--- a/now.xlsx
+++ b/now.xlsx
@@ -567,56 +567,45 @@
       <c r="C2" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲并接受主持人周琦提问。会议围绕“走向多极化”主题展开，王毅提出推动平等有序的世界多极化，并阐述四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅指出，80年前联合国成立时只有51个会员国，如今已有193个国家，多极化是历史必然；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
-在回应主持人周琦关于国际秩序与规则的提问时，王毅表示中国是现行国际秩序的受益者，主张推动秩序朝着更加公正合理的方向发展，并强调应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。王毅指出，在遵守国际法上不能搞双重标准，要尊重各国主权和领土完整，就应该支持中国实现完全统一。
-关于乌克兰危机，王毅表示中国同俄罗斯建立了结盟不对抗、不针对第三方的睦邻友好关系，并反问如果中国不从俄罗斯买油气，哪个国家能提供如此巨量的油气满足中国民众需求。王毅介绍，自2022年2月25日起中方就提出对话协商解决乌克兰危机，习近平主席提出4点主张，中国派特使斡旋，同巴西等南方国家发起和平之友；中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，并认为所有当事方包括利益攸关方都应适时参与和谈进程。
-关于中美关系，王毅表示中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，并阐述对美政策三原则：相互尊重、和平共处、合作共赢。王毅指出，如果美方不愿意相向而行，仍对中国打压遏制，中国必将奉陪到底；中方愿意按照三原则同美方构建稳定健康可持续的双边关系，并引用“天行健，君子以自强不息”“他强任他强，清风拂山岗”等古话表达立场。
+2025年2月，中共中央政治局委员、外交部长王毅在德国慕尼黑安全会议上发表演讲并回答主持人提问。王毅借慕安会报告主题“走向多极化”开篇，指出80年前联合国成立时仅51个会员国、如今已有193个国家，多极化是历史必然，中国主张推动**平等有序的世界多极化**。演讲围绕四点看法展开：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，中国加入了几乎所有普遍性政府间国际组织和600多项国际公约，承担超过20%的联合国会费，去年中国GDP增长5%、对世界经济增长贡献率接近30%。随后，王毅就国际秩序与规则、乌克兰危机、中美关系等议题回应主持人周琦的提问，强调中国是现行国际秩序的受益者，将继续推进劝和促谈，并愿按相互尊重、和平共处、合作共赢三原则同美方构建稳定健康可持续的双边关系。
 # 核心信息
-- **多极化现实**：80年前联合国成立时仅51个会员国，至今已达193个国家；多极化既是历史必然，也正在成为现实（依据：慕安会报告主题「走向多极化」）。
-- **中国多极化主张**：提出推动**平等有序的世界多极化**，系习近平主席提出的重大主张；中国将作为多极体系中的确定性因素，坚定做变革世界中的建设性力量。
-- **四点看法之一·平等相待**：坚持权利平等、机会平等、规则平等，作为建设多极世界的基本原则；主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
-- **四点看法之二·尊重国际法治**：联合国宪章宗旨和原则是国际关系的根本遵循、建设多极世界的重要基石；中国加入几乎所有普遍性政府间国际组织及**600多项国际公约**，从不搞例外主义、不搞合则用不合则弃。
-- **四点看法之三·践行多边主义**：坚持真正的多边主义，倡导共商共建共享的全球治理观；坚定维护联合国权威和地位，承担**超过20%的联合国会费**；切实履行《巴黎协定》，建成世界上最大的清洁发电体系。
-- **四点看法之四·坚持开放共赢**：坚持开放合作，以普惠包容的经济全球化支撑平等有序的世界多极化；反对保护主义、滥加关税、脱钩断链、小院高墙。
-- **中国发展数据**：去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**，担当全球经济增长重要引擎，向世界释放超大规模市场红利。
-- **一带一路对接**：中国愿推动高质量共建「一带一路」，同欧盟「全球门户」战略相互对接。
-- **中欧关系节点**：今年是中欧建交**50周年**，中方愿同欧方深化战略沟通和互利合作。
-- **国际秩序立场**：中国是现行国际秩序的受益者，将按大多数国家愿望推动秩序朝更加公正合理方向发展；应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。
-- **国际法治原则**：在遵守国际法上不能搞双重标准；尊重各国主权和领土完整，就应该支持中国实现完全统一。
-- **中俄关系定位**：中国同俄罗斯建立结盟不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；两国交往属正常国与国交往。
-- **中俄油气贸易**：中国从俄罗斯购买油气系满足民众需求；若中国不从俄罗斯购买，没有其他国家能提供如此巨量油气，且需防范经贸问题政治化、被用作打压中国的工具。
-- **乌克兰危机时间线**：自危机爆发第2天（**2022年2月25日**）起，中方即提出对话协商解决。
-- **乌克兰问题四点主张**：习近平主席提出4点主张——各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。
-- **劝和促谈行动**：中国派特使赴各国斡旋，同巴西等南方国家发起「和平之友」；中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识。
-- **和谈参与范围**：所有当事方包括利益攸关方应适时参与和谈进程；战事发生在欧洲大地，欧洲有必要发挥重要作用，共同探讨均衡、有效、可持续的欧洲安全框架。
-- **对美政策三原则**：对美政策保持连续性和稳定性，不会轻易翻烙饼；遵循习近平主席提出的相互尊重、和平共处、合作共赢三原则。
-- **中美关系应对**：中方愿按三原则同美方构建稳定健康可持续的双边关系；若美方仍对中国打压遏制，中国必将奉陪到底，坚决回击美方单边霸凌行径。
+- **多极化背景数据**：`联合国`成立时（80年前）有51个会员国，现为193个国家；`慕尼黑安全会议`2025年报告主题为「走向多极化」。
+- **中国多极化主张**：推动**平等有序的世界多极化**，系`习近平主席`提出的重大主张；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
+- **四点看法之一·倡导平等相待**：坚持权利平等、机会平等、规则平等，作为建设多极世界的基本原则；`慕安会`近年邀请更多全球南方国家出席会议。
+- **四点看法之二·尊重国际法治**：`联合国宪章`宗旨和原则是国际关系根本遵循；中国加入几乎所有普遍性政府间国际组织和**600多项**国际公约，从不搞例外主义、不搞合则用不合则弃。
+- **四点看法之三·践行多边主义**：中国承担超过**20%**的`联合国`会费；切实履行`巴黎协定`，建成世界上最大的清洁发电体系；提出并落实`全球发展倡议`、`全球安全倡议`、`全球文明倡议`。
+- **四点看法之四·坚持开放共赢**：以普惠包容的经济全球化支撑平等有序的世界多极化；中国愿推动高质量共建`一带一路`，同欧盟`全球门户`战略相互对接。
+- **中国经济数据**：2024年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**；中国向世界释放超大规模市场红利。
+- **中欧关系节点**：2025年系中欧建交**50周年**；中方愿同欧方深化战略沟通和互利合作。
+- **乌克兰危机中方立场**：2022年2月25日（危机爆发第2天）中方即提出对话协商解决；`习近平主席`提出4点主张——各国主权领土完整应得到尊重、`联合国宪章`应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。
+- **劝和促谈行动**：中方派出特使赴各国斡旋；同巴西等南方国家发起`和平之友`；乐见一切和平努力，包括美国同俄罗斯达成的共识；认为所有当事方及利益攸关方应适时参与和谈进程。
+- **中美关系政策**：中国对美政策保持连续性和稳定性；遵循`习近平主席`提出的**相互尊重、和平共处、合作共赢**三原则；愿按三原则同美方构建稳定健康可持续的双边关系。
+- **中美关系底线**：如美方对中国打压遏制，中方必将奉陪到底，坚决维护国家主权、尊严和正当发展权利，坚决回击美方单边霸凌行径。
 # 官方表态
-**中国外交部**：王毅在慕尼黑安全会议上发表演讲，阐述中国对多极世界的立场与主张。
-- **平等有序的世界多极化**：中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是中国对多极世界的期许；中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。
-- **倡导平等相待**：坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权，这不会导致西方的缺失，而将促进世界的正和。
-- **尊重国际法治**：联合国宪章宗旨和原则是国际关系的根本遵循，也是建设多极世界的重要基石；多极格局不能是无序状态，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈。
-- **维护国际法治权威**：中国加入了几乎所有普遍性的政府间国际组织和600多项国际公约，从不搞例外主义，更不搞合则用、不合则弃；在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
-- **践行多边主义**：联合国是践行多边主义、推进全球治理的核心平台，已经为各国遮风挡雨80年；未来的多极世界更加需要联合国，对于这座大厦应该固本强基，而不是拆梁毁柱。
-- **全球治理主张**：中国坚持真正的多边主义，倡导共商共建共享的全球治理观，坚定维护联合国的权威和地位，承担着超过20%的联合国会费；切实履行巴黎协定，建成了世界上最大的清洁发电体系；提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
-- **坚持开放共赢**：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界；保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己；应当坚持开放合作，以普惠包容的经济全球化来支撑平等有序的世界多极化。
-- **共享发展机遇**：中国愿推动高质量共建“一带一路”，同欧盟的“全球门户”战略相互对接，赋能彼此也赋能世界；中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手。
-- **中欧关系**：今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作，推动世界走向和平、安全、繁荣、进步的光明前景。
+**王毅（中共中央政治局委员、外交部长）**在慕尼黑安全会议上发表演讲，阐述中国对多极世界的立场，提出推动平等有序的世界多极化，并表达四点看法。
+- **倡导平等相待**：主张坚持权利平等、机会平等、规则平等，作为建设多极世界的基本原则；呼吁提升发展中国家在国际体系中的代表性和发言权，认为这不会导致西方的缺失，而将促进世界的正和。
+- **尊重国际法治**：认为联合国宪章宗旨和原则是国际关系的根本遵循，也是建设多极世界的重要基石；主张多极格局不能是无序状态，大国要带头讲诚信、讲法治，坚决摒弃言行不一和零和博弈。
+- **践行多边主义**：坚持真正的多边主义，倡导共商共建共享的全球治理观；主张对联合国这座大厦应固本强基而非拆梁毁柱，对全球难题应共担责任而非唯利是图，对共同挑战应团结应对而非阵营对抗。
+- **坚持开放共赢**：主张以普惠包容的经济全球化支撑平等有序的世界多极化；认为保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己。
+- **关于国际秩序**：中国是现行国际秩序的受益者，要推动这个秩序朝着更加公正合理的方向发展；主张共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，认为这是最大的公约数。
+- **关于遵守国际法**：在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一；中国从不搞例外主义，更不搞合则用、不合则弃。
+- **关于中欧关系**：始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手；愿同欧方用好中欧建交50周年契机，深化战略沟通和互利合作，推动世界走向和平、安全、繁荣、进步的光明前景。
+- **关于中美关系**：中国对美政策保持连续性和稳定性，遵循习近平主席提出的相互尊重、和平共处、合作共赢三原则；愿意按照三原则同美方构建稳定健康可持续的双边关系，但如果美方仍对中国打压遏制，中方必将奉陪到底，坚决维护国家主权、国家尊严和正当发展权利。
 # Q&amp;A环节
-**1. 周琦**：您提到国际秩序，但当前我们看到俄罗斯入侵乌克兰、美国总统威胁使用武力入侵格陵兰和巴拿马、巴勒斯坦人流离失所，中国也被指责违反海洋法和《世界人权宣言》。您即将前往纽约参加安理会会议，您是否仍然相信联合国和《联合国宪章》？是否将推动联合国改革？
-**王毅**：我不愿意回答周琦先生的提问，你的提问涉及秩序和规则两个关键词。真正要挑战秩序、毁约退群的国家已经出现，而中国是在现行国际秩序中发展起来的，是受益者，要推动秩序朝着更加公正合理的方向发展。我们应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数。只要认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议和构建人类命运共同体理念，希望各国超越历史文化社会制度意识形态的不同，共同建设好命运与共的地球村。
-**2. 周琦**：2022年慕安会前几天您曾表示任何国家的主权、独立和领土完整都应得到尊重，乌克兰也不例外。如今俄罗斯已成为中国的一个"加油站"，中国对乌克兰有很大影响力。您是否可能减少从俄罗斯购买天然气、降低价格或停止输送军民两用物资，以施压俄罗斯结束战争？
-**王毅**：中国同俄罗斯是两大邻国，建立了结盟不对抗、不针对第三方的睦邻友好关系。如果中国不从俄罗斯买油气，哪个国家能提供如此巨量的油气满足中国民众需求？那是不可能的，也是不保险的，因为常有国家把经贸问题政治化，当做打压中国的工具。中国在乌克兰问题上的立场是主张一切争端和冲突通过对话寻求政治解决。从2022年2月25日起，中方就提出对话协商解决。习近平主席提出4点主张：各国主权领土完整应该得到尊重，联合国宪章应该得到遵守，各国合理安全关切应该得到重视，一切致力于和平的努力都应该得到支持。我们派特使去各国斡旋，同巴西等南方国家发起和平之友。中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识。所有当事方包括利益攸关方都应适时参与和谈进程，欧洲更有必要为此发挥重要作用。
-**3. 周琦**：时间有限，请您简要展望中美关系将如何发展。
-**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不同是各自人民做出的选择，想改造或颠覆对方不切实际。中方愿意按照三原则同美方构建稳定健康可持续的双边关系。如果美方不愿意相向而行，仍对中国打压遏制，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边和霸凌行径。中国有句古话：天行健，君子以自强不息；他强任他强，清风拂山岗。我们对中美关系的未来充满信心，中美共同努力的方向就是相互尊重、和平共处、合作共赢。</t>
+**1. 主持人（周琦）**：您提到国际秩序，我注意到各方对联合国宪章存在质疑——俄罗斯入侵乌克兰、美国总统威胁使用武力入侵格陵兰和巴拿马、巴勒斯坦人流离失所，中国也被指控违反海洋法和《世界人权宣言》。您即将前往纽约出席安理会会议，您是否仍相信联合国和联合国宪章？宪章改革在您的优先事项中排多高？
+**王毅**：你的提问涉及秩序和规则两个关键词。关于秩序，这几年有人说中国要改变秩序、另起炉灶，但现在真正挑战秩序、毁约退群的国家已经出现，欧洲朋友们每天都在感受阵阵寒意。中国是在现行国际秩序中发展起来的，是受益者，我们要做的是按照大多数国家愿望推动秩序朝更加公正合理的方向发展。关于规则，我们起码应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。只要认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，以及构建人类命运共同体理念，希望各国超越历史文化社会制度意识形态差异，同舟共济，共同建设好地球村。
+**2. 主持人（周琦）**：2022年慕安会前几天您曾表示任何国家的主权、独立和领土完整都应得到尊重和维护，乌克兰也不例外。如今俄罗斯已成为中国的一个加油站——带军队的加油站，中国对乌克兰有很大影响力。在各方加大压力推动结束战争之际，中国能否从自身一侧切断俄罗斯供气、降低价格或停止部分军民两用物资，以加大对俄施压？
+**王毅**：中国同俄罗斯是两大邻国，有着漫长边界，两国关系经历过曲折后吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。关于中国是否可以不从俄罗斯买油气——如果中国不从俄罗斯买，哪个国家能提供如此巨量油气满足中国民众需求？那不可能，也不保险，因为常有国家把经贸问题政治化、当作打压中国的工具，我们不会允许这种情况，要为人民负责任。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。我们以此为遵循推进劝和促谈，派出特使斡旋，同巴西等南方国家发起"和平之友"。中方乐见一切和平努力，包括美国同俄罗斯达成的共识，同时认为所有当事方和利益攸关方都应适时参与和谈进程。这场战事发生在欧洲大地上，欧洲更有必要发挥重要作用，共同探讨欧洲长治久安，找到均衡、有效、可持续的欧洲安全框架。
+**3. 主持人（周琦）**：时间有限，能否简要预告您对中美关系将如何发展的看法？
+**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。我们的对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不一样，是各自人民做出的选择，想改造或颠覆对方不切实际。相互尊重是中美交往的前提，和平共处理所当然，中美两个大国总不能冲突起来，那将殃及整个世界。合作共赢是因为国际社会期待中美合作，全球性挑战需要中美携手应对。中方已准备好按照三原则同美方构建稳定、健康、可持续的双边关系，希望美方相向而行；但如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼，新中国就是在战胜各种艰难险阻中发展壮大起来的。我们对世界前途和中美关系未来都充满信心，中美只有一个共同努力方向，就是相互尊重、和平共处、合作共赢。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>46.5</v>
+        <v>45.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/4263</t>
+          <t>7004/3746</t>
         </is>
       </c>
     </row>
@@ -783,85 +772,94 @@
       <c r="C3" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-本次直播由电子科技大学电子科学与工程学院面向考生和家长举办，主持人串场，段院、柳教授、张教授、李天明教授及在读博士田雨桐依次介绍学院整体情况、电子信息材料与元器件、电磁场与微波技术、电路与系统、物理电子学等学科方向，并分享学生视角的择校建议。学院现有本科生1545人、研究生1975人，教师302人（含两院院士2人、领军人才19人、青年人才28人），近5年科研经费到账稳定在3~4亿元，牵头获国家科技奖励11项。
-学院电子科学与技术为国家重点一级学科，下设5个二级学科方向，拥有3个国防特色学科；建有2个国家级平台、4个国际合作平台、7个省部级科研平台，共20个科研团队，其中年度经费过千万元团队15个、过亿元团队1个。电子信息材料与元器件方向依托2个国家级平台，科研面积2万余平米，获国家技术发明等奖项7项；电磁场与微波技术学科始于1956年，拥有6个团队，多项成果应用于雷达、通信等领域；物理电子学方向每年到校科研经费接近2亿元，为学院最多，是国际上最大的真空器件研究中心。
-学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群（群号978499108）及时发布。直播最后公布抽奖口令“一生一世，逐梦未来”，中奖同学需私信后台留下联系方式和收货地址。
+本次招生宣讲直播由电子科技大学电子科学与工程学院主办，面向考生和家长介绍学院整体情况、学科方向与人才培养，并解答夏令营等考生关切问题。学院现有本科生1545人、研究生1975人，教师302人（含两院院士2人、领军人才19人、青年人才28人），拥有2个国家级平台、4个国际合作平台和7个省部级科研平台。学院历史可追溯至1956年建校之初的无线电系、电真空器件系和无线电零件系，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年又成立集成电路学院。电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。科研方面，近5年科研经费到账稳定在3~4亿元，以纵向项目为主、横向为辅，牵头获国家科技奖励11项，发表高水平论文2000余篇，申请专利1600余件、授权1300余件。学院共有20个科研团队，其中年度经费过千万元的团队15个、过亿元团队1个。
+电子信息材料与元器件方向以材料为基础、器件为核心、应用为目标导向，拥有邓龙江院士领导的电磁辐射控制材料与技术团队（年均到账经费3000多万元）和张怀武教授领导的磁电薄膜与微型器件团队（年均到账经费2000余万元），依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室，科研面积2万余平米，获国家技术发明等奖项共计7项。电磁场与微波技术学科始于1956年，由林卫干先生和谢楚芳先生创建，包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向，拥有6个团队，硬件平台含中国高校最先进的微波暗室群体。电路与系统学科1981年开始招收研究生，含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向，拥有国家级人才4人。物理电子学是物理学与电子科学与技术的交叉学科，学校方向起源于1956年在前苏联专家帮助下成立的电子控器件专业，经近70年发展，纵向扩展至上游仿真设计、下游系统应用，拥有自主知识产权商用软件MMST和切皮克，并引入人工智能到器件设计。
+该方向每年到校科研经费接近2亿元，为学院最多，是国际上最大的真空器件研究中心，2023年成功举办行业顶级会议，共有9个团队。学生代表田雨桐（2023级电子科学与技术专业博士研究生）从城市、学校、专业、团队、培养、校园生活、奖助体系等角度分享选择电子学院的8个理由，并建议考生先选研究团队再选导师，可通过学院网站和文献检索网站（如IEEE、中国知网）了解导师情况。关于夏令营，段院表示学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群（群号978499108）及时发布。直播最后公布了抽奖口令“一生一世，逐梦未来”（E为字母E），奖品为学校一整套马克杯，中奖同学需私信后台留下联系方式和收货地址。
 # 核心信息与数据
-## 学院概况
-- **历史沿革**：1956年建校之初成立无线电系、电真空器件系、无线电零件系，经1979年、1992年、2001年、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院。
-- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有电磁场与微波军用关键材料、电子元器件等3个国防特色学科。
+## 学院整体情况
+- **历史沿革**：1956年建校之初成立无线电系、电真空器件系、无线电零件系，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院。
+- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。
 - **党建荣誉**：学院党委入选教育部首批全国党建工作标杆院系，荣获全国教育系统先进集体。
-- **本科生培养**：现有本科生1545人，招生专业为工科试验班（电子工程类），含电子科学与技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向。
-- **研究生培养**：现有硕士和博士研究生1975人，学硕/博士招生专业为电子科学与技术，硕士另有材料科学与工程；专业学位博士为电子信息，硕士为电子信息、材料工程。
-## 师资与科研
+- **本科生规模**：现有本科生1545人，招生专业为工科试验班（电子工程类），含电子科学与技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向。
+- **研究生规模**：现有硕士和博士研究生1975人，招生专业：学硕/博士为电子科学与技术，硕士还有材料科学与工程，专业学位博士为电子信息，硕士为电子信息、材料工程。
 - **师资构成**：现有教师302人，其中教研系列139人、科研系列95人、教学系列14人、实验系列21人，教师总数269人，机关33人。
-- **高层次人才**：两院院士2人、领军人才19人、青年人才28人、其他类型人才12人、博士后61人；拥有2个全国高校黄大年式教师团队，2022年获批4个国家自然科学基金创新群体。
-- **科研经费**：近5年科研经费到账稳定在3~4亿元之间，项目构成以纵向项目为主、横向项目为辅。
-- **科研成果**：牵头获国家科技奖励11项，近5年发表高水平学术论文2000余篇，申请专利1600余件、授权1300余件。
+- **高层次人才**：两院院士2人、领军人才19人、青年人才28人、其他类型人才12人、博士后61人。
+- **科研经费**：近5年科研经费到账稳定在3~4亿元，以纵向项目为主、横向项目为辅。
+- **科研成果**：牵头获国家科技奖励11项，近5年发表高水平论文2000余篇，申请专利1600余件、授权1300余件。
 - **科研团队**：共有20个科研团队，年度经费过千万元的团队15个，其中过亿元团队1个。
-- **科研平台**：拥有国家电子辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室2个国家级平台，4个国际合作平台，7个省部级科研平台；国际交流方面共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
+- **科研平台**：拥有国家电子辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室2个国家级平台，4个国际合作平台，7个省部级科研平台。
+- **教师团队**：拥有2个全国高校黄大年式教师团队，2022年获批4个国家自然科学基金创新群体。
 ## 电子信息材料与元器件方向
-- **方向定位**：以电子材料与电子器件为核心，以材料为基础、器件为核心、应用为目标导向，涉及电子材料、器件、电路的设计研制生产和应用。
+- **方向内涵**：以电子材料与电子器件为核心，以材料为基础、器件为核心、应用为目标导向，涵盖电子材料、器件、电路的设计研制生产和应用。
 - **产业背景**：2021年中国集成电路电子产品进口额度达2.8万亿元，约为原有进口量的1.7倍；先进电子材料、元器件、电路系统等电子产品是我国最紧迫的卡脖子问题之一。
-- **应用领域**：应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域，达到万亿美元量级；元器件发展趋势为微型化、片式化、集成化、薄膜化、智能化，强调材料和器件一体化。
+- **应用领域**：电子产品应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域，达到万亿美元量级。
+- **发展趋势**：元器件向微型化、片式化、集成化、薄膜化、智能化方向发展，强调材料和器件一体化。
 - **邓龙江院士团队**：电磁辐射控制材料与技术团队现有研究人员19人（正高13人、副高15人），发表论文300余篇，承担课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步或技术发明二等奖共3项。
-- **张怀武教授团队**：磁电薄膜与微型器件团队现有研究人员17人（正高15人、副高2人），开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担课题100余项，获科技进步二等奖共3项，发表SCI论文400余篇，年均到账经费2000余万元。
-- **国家级平台**：国家电磁辐射控制材料工程技术研究中心（历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级）和电磁薄膜与集成器件全国重点实验室（2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建）。
+- **张怀武教授团队**：磁电薄膜与微型器件团队现有研究人员17人（正高15人、副高2人），承担课题100余项，获科技进步二等奖共3项，发表SCI论文400余篇，年均到账经费2000余万元。
+- **国家级平台**：依托国家电磁辐射控制材料工程技术研究中心（历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级）和电磁薄膜与集成器件全国重点实验室（2006年依托三个部级重点实验室筹建）。
 - **研究条件**：科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备或系统500余台套；材料制备设备约50余台套、微纳加工设备30台套、微观表征设备10余台套、性能测试设备50余台套。
-- **奖项与毕业生**：获国家技术发明等奖项共计7项；毕业生去向包括英特尔、中芯国际、华为、德州仪器等企业及高校科研院所。
-- **学生代表成果**：在读学生杨伟豪以第一作者在自然电子、自然通讯各发表一篇论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；黄飞获2018年四川省优秀毕业生并获斯坦福攻读博士全额奖学金；李凤霞读博期间发表论文16篇（一作6篇）；严巍获华为光产线优秀合作项目奖、21届王大珞光学奖，以优秀青年学者身份加入苏州大学；万位现任河北美泰电子科技公司副总，采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
+- **奖项成果**：获国家技术发明等奖项共计7项。
+- **毕业生去向**：包括英特尔、中芯国际、华为、德州仪器等企业及高校科研院所。
+- **学生代表成果**：在读学生杨伟豪以第一作者在自然电子、自然通讯各发表一篇论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；黄飞获2018年四川省优秀毕业生并获斯坦福攻读博士全额奖学金；李凤霞读博期间发表论文16篇（一作6篇）；严巍获华为光产线优秀合作项目奖、21届王大珞光学奖，以优秀青年学者身份加入苏州大学；万位现任河北美泰电子科技公司副总，采用MEMS工艺研制出SIW环形器隔离器，实现高性能非互易器件产业化。
 ## 电磁场与微波技术、电路与系统方向
-- **专业构成**：电磁场与微波技术包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
-- **历史沿革**：电磁场与微波技术学科始于1956年，由林卫干先生和谢楚芳先生创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类学科。
-- **科研团队**：电磁场与微波技术有6个团队，包括电磁辐射与散射、毫米波技术与系统应用、微波毫米波集成电路与系统、电磁兼容技术、微波测试与成像技术、无线技术与集成系统。
-- **学科平台**：含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室；硬件平台拥有中国高校最先进的微波暗室群体及微波毫米波太赫兹仿真测试平台。
-- **天线与电磁兼容成果**：杨世文教授团队研究四维天线阵列技术，成果应用于中电14所某大型机载相控阵雷达；在强耦合超宽带相控阵方面取得进展；樊勇教授团队研究毫米波平面集成天线，应用于毫米波通信雷达系统；李恩教授团队在微波毫米波测量技术方面有60多年技术积累，突破众多技术封锁。
-- **电磁测井与计算电磁学**：杨世文教授团队在电磁测井仪器方面获国家科技进步二等奖一项，成果在中海油推广应用；其计算电磁学算法被评为20世纪十大算法之一。
-- **微波毫米波芯片与系统**：延波教授团队在微波毫米波太赫兹芯片研究方面获国家科技重大专项及军科委支持，应用于新一代高速通信系统；在微波毫米波器件与系统方面取得固态合成功率源、天线阵列、扩电网络等成果；在微系统技术方面取得三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端等进展。
-- **太赫兹成果**：樊勇教授团队成功研制0.22太赫兹、0.34太赫兹、0.42太赫兹雷达成像系统，实验平台分辨率小于1厘米；太赫兹通信成果在2023年成都大运会田径项目中成功示范应用。
-- **电路与系统学科**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站；含教育部国际合作联合实验室、国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
-- **人才培养**：连续三年获全国大学生集成电路创新创业大赛奖项，荣获华为优秀合作项目奖、研究生优秀导学团队提名奖；就业领域包括华为、中兴等行业领军企业及各大研究所、高校。
+- **电磁场与微波技术细分**：包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向。
+- **电路与系统细分**：包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
+- **学科历史**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生共同创建；形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业两个方向，所属一级学科电子科学与技术入选双一流A类学科。
+- **研究团队**：电磁场与微波技术有6个团队——电磁辐射与散射、毫米波技术与系统应用、微波毫米波集成电路与系统、电磁兼容技术、微波测试与成像技术、无线技术与集成系统。
+- **学科平台**：含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室；硬件平台拥有中国高校最先进的微波暗室群体及先进的微波毫米波太赫兹仿真测试平台。
+- **天线方向成果**：杨世文教授团队研究四维天线阵列技术，成果应用于中电14所某大型机载相控阵雷达；在强耦合超宽带相控阵方面取得进展。
+- **毫米波天线成果**：樊勇教授团队研究毫米波平面集成天线，应用于毫米波通信雷达系统。
+- **测量技术成果**：李恩教授团队在微波毫米波测量技术方面有60多年技术积累，突破众多技术封锁；杨世文教授团队在电磁测井仪器方面获国家科技进步二等奖一项，成果在中海油推广应用。
+- **太赫兹芯片成果**：延波教授团队在微波毫米波太赫兹芯片研究方面获国家科技重大专项及军科委支持，应用于新一代高速通信系统；在微系统技术方面取得三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端等进展。
+- **电路与系统学科**：1981年开始招收研究生，1988年成立首批博士后流动站，含教育部国际合作联合实验室及国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
+- **车地通信成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制。
+- **毫米波芯片成果**：康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统和雷达系统研制成果。
+- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，荣获华为优秀合作项目奖、研究生优秀导学团队提名奖；就业领域包括华为、中兴等领军企业及各研究所、高校。
 ## 物理电子学方向
 - **学科定义**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学，典型应用包括微波电子学（产生微波电真空器件）、光电子学（产生光电器件）。
-- **学科特点**：内容不断充实（如量子电子学内容逐渐增加），学科边界不一定清晰（如光电子学也可属光学工程一级学科）；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
-- **发展历程**：起源于1956年建校时在前苏联专家帮助下成立的电子控器件专业，归属电子器件系；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年成立电子科学与工程学院。
-- **纵向扩展**：向上游（仿真设计、数字模拟材料）和下游（系统应用）发展，拥有自主知识产权商用软件MMST和切皮克；引入人工智能到器件设计和电子学应用。
-- **系统应用**：用回旋行波管研制毫米波雷达，用行波管做无线输能系统，用磁控管做微波能干燥系统。
-- **横向发展**：频段从微波上移到毫米波、太赫兹；与医学交叉，利用太赫兹成像提高诊断准确性，利用太赫兹宽频带做保密通信、高速通信。
-- **平台与经费**：拥有3个四川省工程中心或重点实验室，每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心，2023年成功举办行业顶级会议。
-- **团队与学生出口**：物理电子学方向共有9个团队；团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（如公务员）；李天明教授个人每年约2个研究生毕业、1个博士毕业。
-## 学生视角与择校建议
-- **选择理由**：田雨桐为电子学院2023级电子科学与技术专业博士研究生，从城市（成都为四川省会、国家中心城市、新一线城市，英特尔、华为、京东方等巨头汇聚）、学校（电子信息人才培育代名词，有电子信息博物馆记录我国第一台晶体管收音机诞生）、专业（电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一）等角度分享选择理由。
-- **团队与就业**：学院拥有四大学科和19个科研团队；田雨桐所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究；团队硕博毕业生实现100%就业率，就业单位包括民营企业、大型央国企和头部科研院所。
-- **校园生活与奖助**：2021年跨年学校用300架无人机在主楼前拼出UESTC字样；学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金、校园地国家助学贷款和生源地助学贷款等。
-- **择校建议**：先选研究团队再选导师，可通过学院网站和文献检索网站（如IEEE、中国知网）了解导师论文和指导研究生情况，提前沟通交流。
+- **学科特点**：内容不断充实（如量子电子学）、学科边界不一定清晰（如光电子学也可属光学工程一级学科）。
+- **发展历程**：起源于1956年建校时在苏联专家帮助下成立的电子控器件专业，归属电子器件系；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年成立电子科学与工程学院。
+- **纵向扩展**：上游扩展至仿真设计、数字模拟材料，下游扩展至系统应用；拥有自主知识产权商用软件MMST和切皮克；引入人工智能到器件设计和电子学应用。
+- **系统应用**：包括毫米波雷达（用回旋行波管）、无线输能系统（用行波管）、微波能干燥系统（用磁控管）。
+- **横向扩展**：频段从微波上移至毫米波、太赫兹；与医学交叉，利用太赫兹成像提高诊断准确性，利用太赫兹宽频带做保密通信、高速通信。
+- **科研平台与经费**：拥有3个四川省工程中心或重点实验室，参与成立一系列行业协会；每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心，2023年成功举办行业顶级会议。
+- **团队与学生出口**：物理电子学方向共有9个团队；团队学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他（如公务员）。
+## 学生视角分享
+- **城市优势**：成都是四川省会、国家中心城市、新一线城市、国家历史文化名城、古蜀文明发祥地、中国十大古都之一，电子信息产业发达，英特尔、华为、京东方等巨头汇聚。
+- **学校优势**：电子科大是我国电子信息人才培育的代名词，有电子信息博物馆记录我国第一台晶体管收音机的诞生，构建了最完整的电子信息学科群。
+- **专业优势**：电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一。
+- **团队培养**：学院拥有四大学科和19个科研团队；田雨桐所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究。
+- **就业情况**：团队硕博毕业生实现100%就业率，就业单位包括民营企业、大型央国企和头部科研院所。
+- **校园生活**：2021年跨年学校用300架无人机在主楼前拼出电子科大英文简称UESTC字样。
+- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金、校园地国家助学贷款和生源地助学贷款等。
+- **择校建议**：先选研究团队再选导师，可通过学院网站和文献检索网站（如IEEE、中国知网）检索导师论文和指导研究生情况，提前沟通交流。
 # 各方立场与诉求
-- **段院（学院负责人）**：面向考生和家长介绍学院整体情况，涵盖历史沿革、学科设置、师资队伍、科研平台与成果、人才培养等，意在吸引优秀生源报考；回应夏令营问题时说明学院计划今年举办、时间待定，相关信息将通过QQ群发布。
-- **柳教授（电子信息材料与元器件方向）**：介绍该方向以材料为基础、器件为核心、应用为目标导向，强调先进电子材料、元器件、电路系统等是我国最紧迫的卡脖子问题之一，并展示两个研究团队的规模、经费与获奖情况，呼吁考生报考该方向。
-- **张教授（电磁场与微波技术、电路与系统方向）**：介绍两个学科方向的研究内容、6个科研团队及多项应用成果（如四维天线阵列应用于中电14所机载相控阵雷达、太赫兹通信在成都大运会示范应用等），展示学科实力以吸引考生。
-- **李天明教授（物理电子学方向）**：介绍物理电子学的学科定义、学校近70年发展历程、研究方向拓展（太赫兹成像、保密通信、医学诊断等）及学生出口情况，说明团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他。
-- **田雨桐（在读博士）**：从学生视角分享选择电子学院的8个理由，包括城市产业环境、学校学科群、专业A+评估、团队实力、校园生活、奖助体系等，并给出择校建议——先选研究团队再选导师，可通过学院网站和文献检索网站了解导师情况。
-- **主持人**：串场引导各环节，收集弹幕区考生问题，就夏令营安排向段院提问，并组织抽奖互动；段院回应夏令营计划举办但时间待定，建议考生加入QQ群获取后续信息。
+- **段院（学院负责人）**：面向考生和家长介绍学院整体情况，回应夏令营咨询，明确学院计划今年举办夏令营活动，但具体时间待定，相关信息将通过QQ群（群号978499108）及时发布。
+- **柳教授**：介绍电子信息材料与元器件方向，强调该方向以材料为基础、器件为核心、应用为目标导向，指出先进电子材料、元器件、电路系统等是我国最紧迫的卡脖子问题之一，并展示团队实力与毕业生去向，呼吁考生报考该方向。
+- **张教授**：介绍电磁场与微波技术和电路与系统两个专业方向，展示学科历史、研究团队、科研成果与人才培养成效，表达对考生加入学院的欢迎。
+- **李天明教授**：介绍物理电子学方向，说明学科定义、学校发展历程、研究方向及学生出口，强调该方向每年科研经费接近2亿元、为学院最多，是国际上最大的真空器件研究中心。
+- **田雨桐（在读博士生）**：从学生视角分享选择电子学院的8个理由，涵盖城市、学校、专业、团队、培养、校园生活、奖助体系等，并建议考生先选研究团队再选导师，可通过学院网站和文献检索网站（如IEEE、中国知网）了解导师情况。
+- **主持人**：串联各环节，收集弹幕区考生问题，就夏令营安排向段院提问，并组织抽奖互动，公布抽奖口令“一生一世，逐梦未来”（E为字母E），奖品为学校一整套马克杯。
 # 达成共识
-- **夏令营安排**：段院确认电子学院**计划今年举办夏令营活动**，具体时间与形式待定，相关信息将通过学院QQ群及时发布。
-- **信息发布渠道**：学院QQ群号**978499108**，考生和家长可入群获取夏令营及招生后续信息。
-- **直播互动确认**：本场直播抽奖口令为「一生一世，逐梦未来」（E为字母E），奖品为电子科技大学logo马克杯一套（含勺子和杯盖），中奖同学需私信后台留下联系方式和收货地址。
+- **夏令营安排**：段院明确**电子学院计划今年举办夏令营活动，具体时间待定**，相关信息将通过学院QQ群及时发布。
+- **信息发布渠道**：学院QQ群号确认为**978499108**，考生和家长可扫码或搜索群号加入，用于获取夏令营等后续通知。
+- **直播互动承诺**：主持人公布抽奖口令为「一生一世，逐梦未来」（E为字母E），奖品为学校一整套马克杯（含电子科技大学logo、勺子和杯盖）；中奖同学需私信后台留下联系方式和收货地址，奖品将派送至家门口。
 # 待协调事项与后续
 ## 待协调事项
-- **夏令营具体时间与形式**：电子学院计划今年举办夏令营活动，时间待定，相关信息将通过学院QQ群及时发布。
+- **夏令营具体时间与形式**：段院表示电子学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群及时发布。
 ## 后续安排与参与方式
-- **学院咨询QQ群**：群号978499108，考生和家长可扫码或搜索群号加入，咨询学院招生、夏令营等相关事宜。
-- **夏令营信息发布渠道**：学院计划今年举办夏令营，具体时间确定后将在QQ群内及时发布，请考生和家长留意群通知。
-- **直播抽奖兑奖方式**：中奖同学需私信直播后台，留下联系方式和收货地址，奖品（电子科技大学logo马克杯一套，含勺子和杯盖）将派送至家门口。
-- **面对面交流预告**：学院期待在夏令营或研究生入学时与考生和家长进行面对面沟通交流。</t>
+- **咨询渠道**：学院QQ群号978499108，考生和家长可扫码或搜索群号加入，进行详细咨询和了解。
+- **夏令营信息发布**：夏令营相关安排确定后将在QQ群内及时发布，请感兴趣的同学关注群消息。
+- **直播抽奖兑奖**：中奖同学需私信后台留下联系方式和收货地址，奖品为电子科技大学一整套马克杯（含学校logo、勺子和杯盖），将在不久后派送。
+- **抽奖口令**：直播抽奖口令为「一生一世，逐梦未来」（E为字母E），中奖名单已当场截屏公布。</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>99.3</v>
+        <v>101.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/5988</t>
+          <t>13887/6449</t>
         </is>
       </c>
     </row>
@@ -1398,132 +1396,143 @@
       <c r="C4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-2023年度总结暨年终奖颁发年会于年末召开，由老板主持，围绕全年经营数据、年终奖发放标准、员工逐一点评、部门评价与展望、颁奖及抽奖等环节展开。会议核心基调为：公司总量在提升，但成本控制差、结余到账下滑，老板承认管理问题并承诺明年反思改进。关键数据包括：年终奖转账总额226,000元，全年实打实支出390万元（含人员工资、外援配音字幕、租机器），利润率约24%或27%，老板个人比去年少拿约10万元并承担亏损100万元。
-会议预期目标为总结2023年发展状况、公布年终奖并表彰员工，实际结果基本达成：年终奖按入职时长与表现发放，共颁发5项奖（6人获奖），并对短视频、执行、商务三个部门逐一评价。老板指出成本控制差是最大问题，根源在于老板管理问题，明年开会再讨论；同时明确年终奖和颁奖对后期有所侧重，这是唯一愿意解释的发放原因。
+公司于2023年末召开年度总结会，由老板主持，围绕2023年经营数据、年终奖发放标准、员工个人评价、部门总结展望、颁奖及抽奖等环节展开。会议核心基调为肯定公司总量提升与员工付出，同时直面成本控制差、账号未变现等突出问题，并明确部分事项留待明年会议再议。
+会议公布的关键数据包括：年终奖总额226,000元，成本支出390万元（含人员工资、外援配音、字幕、租机器），利润率24%或27%；最高工资（含年终奖）两三人达到20万以上，平均工资到手1万多元；2023年平时工资较去年提高25万左右，年终奖比去年多13万至12万（原文表述为“1312万多”，按上下文理解为比去年多十余万）；干满一年的员工由去年四五人增至今年12人。老板指出成本控制差是最大问题，根源在于老板管理问题，并提到公司结余到账往下跑、有百来万没收回来，老板个人比去年少拿10万左右、承担风险亏了100万。
 # 全年结果与表彰
 ## 经营数据与口径
-- **年终奖总额**：2023年年终奖转账总额为226,000元。
-- **全年支出**：实打实花出去的钱（含人员工资、外援配音、字幕、租机器）共390万元。
-- **利润率**：约24%或27%，老板认为非常不可观。
-- **最高工资**：两三个人包括年终奖拿到手达到20万以上。
-- **平均工资**：员工平均拿到手1万多元。
-- **人工支出变化**：平时工资拿到手比去年提高25万左右；年终奖比去年多13万至12万多。
-- **人员规模**：干满一年的员工去年四五个人，今年12个人。
-- **公司结余**：总量在提升，但结余到账往下跑，还有百来万没收回来。
-- **老板个人收入**：比去年少拿10万左右，承担风险亏损100万。
+- **年终奖总额**：226,000元，个人数额不一一公布。
+- **成本支出**：390万元（含人员工资、外援配音、字幕、租机器），老板称成本控制非常差是最大问题。
+- **利润率**：24%或27%，老板认为非常不可观。
+- **最高工资**：含年终奖，两三人到手达到20万以上。
+- **平均工资**：到手1万多元。
+- **人工支出**：2023年平均人工支出相对提高，平时工资到手提高25万左右。
+- **年终奖对比**：比去年多1312万多；干满一年员工去年四五人，今年12人。
+- **公司结余**：总量提升，但结余到账往下跑，有百来万没收回来。
+- **老板个人**：比去年少拿10万左右，承担风险亏了100万。
 ## 制度与标准
-- **年终奖发放标准**：刚入职两三个月至半年以内的发红包，去年600、800元，今年约1000元；干满一年的以一个月基本工资为基准，表现好会更高；超过一年主要考虑当年表现，干的久且满意者有高预算，实际拿到两三万，大几万也有预算。
-- **破格情况**：虽然只干了半年，也有给一个月以上年终奖的破格案例。
-- **奖项评选规则**：奖项评选为2选1或3选1，具有竞争性；没拿到不代表能力不行，但至少证明不突出。
-- **年终奖侧重**：年终奖和颁奖对后期有所侧重，老板表示这是唯一愿意解释的原因。
-- **额度调整**：因林海腾对刘腾宇的肯定，在既定标准上再拉一档。
+- **年终奖发放标准**：刚入职两三个月或半年以内发红包，去年600、800元，今年可能1000元左右。
+- **满一年员工**：以一个月基本工资为基准，无大问题会比基准高甚至更高。
+- **超过一年员工**：不多考虑年限，主要考虑年度表现。
+- **年限久且满意**：预算可给大几万，但需给老板一个理由。
+- **额度问题**：明年开会再讨论。
+- **奖项评选**：认真讨论、严肃对待，公平公正，与任何人非亲非故。
+- **奖项竞争性**：相同级别框出两三人，2选1或3选1，未拿到不代表能力不行，但证明不突出。
 ## 奖项与表彰
-- **最佳新人奖**：颁给红叶子（入职两三个月，10月入职、11月转正）和张扬（公司邀请来的人才，来了半年左右）。
-- **最佳进步奖**：颁给欧阳小元，技术进步明显，从去年到今年跑了一截。
+- **最佳新人奖**：颁给红叶子、张扬，各含红包。
+  - 红叶子：政委给予非常高的评价，既懂技术又懂英语，有把事情做好的精神头。
+  - 张扬：工作能力、工作态度、实际作用均获认可，无信息差。
+- **最佳进步奖**：颁给欧阳小元，技术进步明显，跑了一截。
 - **后期独挡一面奖**：颁给市井，能完美胜任课程、微电影、MV、快剪等各类后期，政委给予非常高的评价。
-- **最佳员工奖**：颁给游腾宇，含金量最高，从纪律、执行、职业态度、技术能力、出活各方面综合评定，奖金稍多。
-- **特别贡献奖**：颁给李海涛，奖金为单项奖中最多，因辛苦程度最大、最操心，对运营层面有重要意义。
+- **最佳员工奖**：颁给刘腾宇，含金量最高，从纪律、执行、职业态度、技术能力、出活各方面综合评选，奖金稍多一点。
+- **特别贡献奖**：颁给林海腾，奖金是单项奖中最多的，因其辛苦程度最大、最操心，承担上传下达、执行救火等运营层面重要工作。
 ## 环节与福利
-- **颁奖仪式**：今年认真对待仪式感，证书为皮质，40元一本含设计费，字体经过认真核对。
-- **红包**：颁奖时附带红包，金额相对可观。
-- **抽奖**：共15个奖品，包括充电宝（价值79元）、观影券（价值30元）、洗头膏（价值七八十元）；一等奖充电宝、二等奖观影券、三等奖洗头膏。
-- **100元红包**：老板手写一张抽奖券，抽中者现场发100元红包。
-- **群红包**：林彦腾发200元红包在群里，老板转给林彦腾。
-- **报销福利**：当天看电影或吃饭在一定额度内可酌情报销，仅限当天有效。
+- **证书**：皮质证书40元一本（含设计费），字体认真核对过，选用了苍耳青和字体。
+- **红包**：老板自己写了一个100元红包，抽中者现场发放。
+- **抽奖**：共15个奖品，含一等奖充电宝价值79元、三等奖观影券价值30元、洗头膏价值七八十元（年后拿）。
+- **报销福利**：当天看电影或吃饭，一定额度内可酌情报销，仅限当天。
+- **群红包**：林彦腾发200元红包在群里，老板转账给他。
+- **年终奖侧重**：发年终奖和奖项时侧重于后期，后期比前期少一截是事实，老板称这是唯一愿意解释的原因。
 ## 人员评价
 ### 红叶子
-- **技术能力**：政委给予非常高的评价，认为很难招到这样的人才，既懂技术又懂英语，有把事情做好的精神头。
-- **工作态度**：填工资表时在意见栏会写如何把项目做得更好的建议，认真对待工作。
+- **综合评价**：入职两三个月（10月入职，11月转正），政委给予非常高的评价，称很难招到既懂技术又懂英语、有把事情做好的精神头的人才。
+- **工作态度**：填工资表时在意见栏写如何把项目做得更好的建议，认真对待工作。
 ### 郭东辉
-- **运营能力**：非常有经验的运营，克服了本不应该面对的一些困难，公司限制了他的一些发挥，老板表示歉意。
-- **账号数据**：视频号粉丝从3月1日的700人增长至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万。
-- **账号变现**：自评达到7.5分（满分10分），重点项目未完成。
-- **直播情况**：视频号直播4-5场，平均在线人数5000+，前100人平均在线50分钟以上。
-- **坚持过程**：6月20日前潘老师多次（约10次）提醒去找工作，因其他公司挖角破釜沉舟说服潘老师外出拍摄，账号开始有起色。
+- **运营能力**：干满一年的运营，非常有经验，克服了本不应面对的困难。
+- **账号数据**：视频号粉丝从719人涨到8万，小红书从2000+涨到6.4万，抖音从2000+涨到5.7万，B站从3.1万涨到7.6万，均从6月20日外出拍摄视频开始起色。
+- **账号变现**：达到7.5分（满分10分），重点项目未完成；直播在视频号直播4-5场，平均在线人数5000人以上。
+- **坚持过程**：6月20日前潘老师多次（约10次）提醒出去找工作，郭东辉坚持不放弃，破釜沉舟说服潘老师外出拍摄。
+- **公司限制**：老板表示公司可能限制了其发挥，应表示歉意。
 ### 刘腾宇
-- **职业性**：对老板和客户回复都非常专业，沟通上比老板说得还好。
+- **职业性**：对老板和客户回复都非常专业，沟通能力强。
 - **纪律性**：几乎没有迟到，请假严格按规定提前告知并安排工作。
-- **客户反馈**：宁波城市项目客户罗峰向政委表示，如果不是这个小姑娘做得好，早投诉了。
-- **效率**：效率最高，重要活安排给他不会有任何问题。
-- **年终奖**：刚满一年但给老板感觉像干了五六年的老员工，年终奖会让人惊喜，可能翻倍。
-### 欧阳
-- **工作态度**：有认真的工作态度，技术水平有一定学习能力，进步明显。
-- **提升空间**：沟通能力需要再爬坡，总体打分不低。
+- **客户反馈**：宁波城市项目客户罗峰向政委反馈，如果不是小姑娘做得好，早投诉了。
+- **效率**：效率最高且不出问题，老板称重要活安排给刘腾宇就放心。
+- **年终奖**：刚满一年但给老板感觉像干了五六年的老员工，年终奖会翻倍。
+### 欧阳小元
+- **工作态度**：认真，技术水平有一定学习能力，进步明显。
+- **提升空间**：沟通能力需再爬坡。
+- **总体评价**：打分不低，获最佳进步奖。
 ### 徐艺玲
 - **工作质量**：一遍过的非常多，仔细认真，挑不出毛病。
-- **技术进步**：原先只能剪课程，今年剪宣传片类也像模像样。
-- **客户好评**：杨晶项目其他人做不了，客户点名让这个小姑娘来做。
+- **技术进步**：原先只能剪课程，今年剪宣传片类像模像样。
+- **课程类**：既有效果又有效率，获好评多；杨晶项目其他人做不了，客户点名让徐艺玲做。
 ### 张文倩
-- **综合能力**：需要沟通能力和专业水平兼备，表现高出老板期待。
-- **项目完成**：宁波项目老板原以为干不了，但人家完成了，出乎意料。
+- **综合能力**：既需要沟通能力也需要专业水平，表现高出老板期待。
+- **项目完成**：宁波项目老板原以为干不了，结果完成，出乎意料。
+- **提升空间**：因年龄和工作年限，经验上有所欠缺，但灵光性能进步。
 ### 市井
-- **技术标杆**：后期方面最好的没有之一，从技术感觉上依然是在座最好的。
-- **品质保证**：从更高品质上来说依然是最好的，攻坚克难的角色。
+- **技术标杆**：后期方面最好的没有之一，依然是技术标杆。
+- **品质**：从更高品质上来说依然是最好的，攻坚克难。
+- **参与项目**：尊重个人意见，必要的后期会议也参加了。
 ### 钱德峰
-- **辛苦程度**：后半年拍摄非常密集，两个月连轴转没有一天休息。
-- **额外贡献**：安排拍摄人员、建议办停车券、关心设备更新，不是本职工作也关心公司发展。
-- **提升空间**：期待更强的执行能力，项目或沟通谈判方面。
+- **拍摄强度**：元老级人物，后半年拍摄密集，两个月连轴转没有一天休息。
+- **工作安排**：除自己拍摄外，还安排拍摄人员，操心较多。
+- **关心公司**：提出办停车券、设备更新等运营层面建议，非本职工作也关心公司发展。
+- **提升空间**：期待更强的执行能力。
 ### 徐武安
-- **工作表现**：比较灵光，眼里有活，警察学院驻场一个人孤苦伶仃非常辛苦。
-- **客户反馈**：刚去时被认为经验欠缺，后来客户觉得误会了，认为挺灵。
-- **技术水平**：拍摄技术水平好于后期技术水平。
+- **工作态度**：灵光、眼里有活，警察学院驻场一人孤苦伶仃，非常辛苦。
+- **客户反馈**：刚去时被认为经验欠缺，后来反馈觉得挺灵。
+- **技术水平**：拍摄和后期技术过关，拍摄技术好于后期。
 ### 宋俊逸
-- **编导能力**：第一个活是宁波两分钟小宣传片，发来文稿后老板觉得这个人是对的，效率不错。
-- **项目完成**：监狱、财经等项目没有出现任何问题，交给他是完全放心的。
+- **编导能力**：刚来两三个月（10月入职），第一个活是宁波两分钟小宣传片，文稿效率高，老板称行家一出手便知有没有。
+- **项目完成**：监狱、财经等项目未出现任何问题，交给其完全放心。
 ### 张扬
-- **人才引进**：公司邀请来的人才，来了半年左右，基本达到期待。
-- **老板评价**：2023年干得最有价值的一件事就是把他招进来。
+- **综合评价**：公司邀请来的人才，来半年左右，职业态度和工作能力有目共睹，基本达到期待。
+- **老板评价**：2023年干到最有价值的事就是招他进来，非常中肯。
 - **待遇**：给了比较有诚意的待遇。
 ### 林海腾
-- **运营作用**：上传下达，传达员工声音，对运营层面有比较重要的作用。
-- **辛苦程度**：半夜或周六周天被侵占最多，最操心，执行层面谁不满意去补救。
+- **运营作用**：上传下达，公司声音通过其传达，后期安排繁重。
+- **辛苦程度**：半夜或周六周天被侵占最多，最操心，执行层面救火、沟通都承担。
+- **评价**：老板和政委商量年终奖时，因林海腾的肯定给刘腾宇拉一档年终奖。
 ### 李国宇
-- **拍摄水平**：在公司算比较高的，能胜任稍高难度的工作。
-- **后期灵性**：剪理工项目第一遍乱七八糟，被逼一顿后完美交差，能听懂指导。
-- **提升空间**：沟通能力需要提升。
+- **拍摄水平**：公司内算比较高，能胜任稍高难度的活。
+- **后期灵性**：能进步能听懂，理工项目第一遍剪得乱，沟通后完美交差。
+- **提升空间**：沟通能力需提升，期待能达到外援段位。
 ### 张启
-- **主观能动性**：表现高于预期，主动联系客户，不是指一步动一步。
-- **老板支持**：老板给的支持比较少，几乎没有项目，后面会考虑给予更多支持和帮助。
+- **综合评价**：干了一年的商务，表现高于老板预期，面试时以为害羞，实际外向玩得开。
+- **主观能动性**：主动联系客户打电话，不是指一步动一步。
+- **老板支持**：老板给的支持较少，几乎没什么项目，后面会考虑给更多支持和帮助。
 # 亮点事项
-- **账号运营突破**：郭东辉负责的短视频账号在2023年实现显著增长，视频号粉丝从3月1日的700人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万；关键转折点是6月20日说服潘老师到室外拍摄对话类视频，此前潘老师已10次提醒其另找工作，郭东辉以破釜沉舟心态坚持推动，并因外部公司挖角而坚定决心。
-- **账号变现初具雏形**：郭东辉自评账号变现程度达7.5分（满分10分），视频号已直播4-5场，平均在线人数5000+，前100人平均在线时长超50分钟；虽暂无课程产品，但已具备变现条件，老板认为账号虽未变现但提升了公司综合实力的软形象。
-- **直播数据亮眼**：视频号直播平均每场在线人数达5000+，前100名观众平均在线时长50分钟以上，为后续课程变现打下用户基础。
-- **员工坚持与成长**：郭东辉在项目困难期坚持不放弃，认为「如果要放弃应该是黄大师那边去说」，并总结出「说服自己最难」的认知收获；其工作方法强调数据支撑，每晚8-9点刷英语老师直播间研究内容与互动，所有决策基于数据而非主观想法。
-- **后期团队整体进步**：林海腾指出今年后期人员分级模糊化，整体效率趋同，制作能力提升，后半年基本都在加班但质量有保障；老板在年终奖中额外补贴加班部分，约一两千元。
-- **新员工超出预期**：红叶子入职两三个月即获政委高度评价，称「很难招到既懂技术又懂英语且有把事情做好的精神头的人才」；宋俊逸入职两三个月，首次安排宁波宣传片任务即快速交付高质量文稿，老板评价「行家一出手便知有没有」。
-- **招聘价值突出**：老板称2023年最有价值的事是招入张扬，其职业态度与工作能力基本达到期待，且能做三维制作，有望解决往年二维三维外包问题。
-- **员工激励创新**：老板为增强仪式感，认真准备皮质证书（40元/本含设计费），设置最佳新人、最佳进步、后期独挡一面、最佳员工、特别贡献五项奖，评选采用2选1或3选1竞争机制；老板表示「每一句每个人的台词，我真的是认真想过的」，体现对员工评价的重视。
-- **跨部门协作认可**：刘腾宇获最佳员工奖，老板评价其职业性、专业性、纪律性均为最好，客户反馈「如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了」；老板因林海腾的肯定为其年终奖再拉一档，可能翻倍。
+- **短视频账号增长超预期**：郭东辉负责的账号从2023年3月1日视频号粉丝719人增长至8万，小红书从2000+涨至6.4万，抖音从2000+涨至5.7万，B站从3.1万涨至7.6万；**转折点是6月20日第一条外出拍摄的对话视频**，此前潘老师曾10次提醒郭东辉「出去找工作吧」，郭东辉以破釜沉舟心情说服潘老师外出拍摄，加上forty加入，项目得以坚持。
+- **账号变现初具成效**：账号变现按满分10分自评达7.5分，课程已上架，直播在视频号进行4-5场，平均在线人数5000人以上，前100人平均在线时长50分钟以上；老板评价「从数据上或前景上起码是向好的」，同行运营者惊讶「你们居然能做这么久」。
+- **员工坚持成为项目关键**：郭东辉在6月20日前多次被建议放弃项目，但坚持「如果要放弃应该是黄大师那边去说」，并主动说服潘老师外出拍摄；老板表示「因为有这样的员工，我要把这个事搞成了才能对得起人家」，员工给予了老板信心。
+- **刘腾宇获最高评价**：老板评价其职业性、专业性、纪律性均为最好，「刚满一年却给老板干了5、6年老员工的错觉」，年终奖在既定标准上因林海腾肯定再拉一档，实际可能翻倍；客户反馈「如果不是你这个小姑娘做得好，你们做得这么慢，早投诉你们了」。
+- **张扬入职被视为年度最有价值事件**：老板称「2023年干到最有价值的一件事就把他招进来」，其职业态度与工作能力基本达到期待，且能做三维包装，**往年二维三维均外包，现可内部解决**。
+- **宋俊逸首次任务即获认可**：入职两三个月，老板安排宁波两分钟宣传片编导任务，文稿「一会儿就发来」，老板评价「行家一出手便知有没有」，后续监狱、财经项目均无问题。
+- **张文倩完成高难度项目**：老板原以为宁波项目「可能就黄了」，但张文倩完成且出乎意料，其岗位需综合沟通能力与专业水平。
+- **市井获「后期独挡一面奖」**：政委搜名半天，意为「课程、微电影、MV、快剪全都能完美解决」，老板称其「依然是我们在座的最好的没有之一」。
+- **红叶子获政委极高评价**：政委称「很难招到这样的一个人才，既懂技术又懂英语，有把事情做好的精神头」，且会在工资表意见栏写如何把项目做得更好。
+- **拍摄团队积极性获认可**：钱德峰后半年拍摄密集，两个月连轴转无一天休息，还主动安排拍摄人员、建议办停车券、更新设备；员工钱德峰指出「喊外援价格差很多」，拍摄小伙子「干活都很得劲」，与外部助理形成对比。
+- **颁奖仪式感增强**：去年李海腾建议公司欠缺仪式感，今年老板认真对待，**证书为皮质、40元一本含设计费**，字体认真校对，奖金相对可观，另设两个洗手包（值七八十元）及老板自写100元红包奖。
 # 不足事项
-- **成本控制极差**：全年实打实支出（含人员工资、外援配音字幕、租机器）达390万元，利润率仅约24%或27%，老板直言“非常不可观”。根因是**老板对成本关心或关注不够，不够雷厉风行，出现问题未及时解决**，属管理问题。
-- **公司结余缩水**：总量在提升，但结余到账往下跑，还有百来万没收回来；老板个人比去年少拿约10万元，并承担风险亏损100万元。
-- **账号变现未完成**：郭东辉自评账号变现程度为7.5分（满分10分），重点项目“账号变现”明确“可以说是没有完成”；直播虽已播4-5场、平均在线5000人+，但“现在没有课程，所以说他是可以进行变现的”，变现条件尚不具备。
-- **拍摄外援成本高**：钱德峰指出“请了很多天的外援”，但“有一些东西我们公司自己人内部就可以搞定”，如“上午谁有空谁去一下，其实就是很简单的按个机位，只要让机器不关机就ok”，然而“这样的人我们公司都凑不出来”；外援与内部拍摄“两边价格是差很多的”。
-- **加班严重、人员不足**：林海腾反映“今年尤其是后半年，基本上都在加班，很少是有一个正常的休息”；老板承认根因是**没有及时招更合适或更合适人数的人员**，属“判断失误”，“人不够是最大的因素”。
-- **拍摄参与度低**：钱德峰提到喊人参与拍摄时“很多人由借口运用一个没空很忙不想去”；老板补充，被问到拍摄任务时直接说“没空”是“非常不职业的”，应至少解释手头工作或勉为其难安排。
-- **老板支持不足**：老板承认对商务部门“给予的支持，或者管理或者是关心其实是不够的”，明年会反思；对张启也坦言“我们做老板来说，给他的支持比较少，他几乎没有什么项目”。
-- **跨部门信息差**：老板指出“跨部门之间可能相互都有点不了解”，如商务会觉得技术“活都是我接的，都是我的功劳”，技术可能觉得商务“就靠一张嘴不说也可以”，需通过员工自述环节来弥补。
-- **员工自评未达预期**：张启自评“2023年就是我自己对我自己的预期的话，我感觉年终对我自己来说，我感觉是没达到我自己的预期的”，原因包括“效率也是一方面”“时间也是一方面”，以及“项目上对同事的沟通和那个和甲方的可能做的不太好”。
+- **成本控制差**：全年实打实花出去的钱（含人员工资、外援配音、字幕、租机器）达 **390 万元**，利润率仅 24% 或 27%，老板直言「非常不可观」；根因是 **老板对成本关心或关注不够、不够雷厉风行，出现问题未及时解决**，属管理层面的根源问题，明年开会再讨论。
+- **公司结余缩水**：2023 年公司总量在提升、员工拿到手的钱在提升，但成本往上跑，公司结余到账往下跑，还有 **百来万没收回来**，实际结余稍微缩水；老板个人比去年少拿约 10 万元，并承担风险亏了 100 万元。
+- **账号未变现**：短视频账号虽在 2023 年各平台涨粉明显（视频号从 719 人涨到 8 万、小红书从 2000+ 涨到 6.4 万、抖音从 2000+ 涨到 5.7 万、B站从 3.1 万涨到 7.6 万），但**账号变现重点项目没有完成**，目前没有课程可售，尚不能变现；老板期待明年账号开始变现并投入更大精力。
+- **拍摄人员不足、外援成本高**：后半年拍摄密集，请了很多天外援，但部分工作公司内部即可完成（如上午谁有空去按个机位、让机器不关机即可），实际却凑不出人；外援与内部人员拍摄价格差很多，且喊人时常被以「没空、很忙、不想去」推脱；老板承认未及时招合适人数是判断失误，明年希望每个人都能参与拍摄。
+- **加班多、休息时间被侵占**：后半年基本都在加班，包括晚上和周末，很少正常休息；根因是**人不够是最大因素**，老板承认未及时招更合适或更合适人数的人员，属判断失误；老板表示明年将更多组织协调，尽可能少侵占大家休息时间。
+- **商务部门支持不足**：商务部门实打实项目约 300 万元左右，基本达到预期，但老板承认给予的支持、管理或关心不够，张启几乎没什么项目，主要靠老板帮忙聊或打理；老板表示明年会反思并给予更多支持帮助。
+- **拍摄与后期收入侧重不一致**：年终奖及奖项发放侧重于后期，后期比前期（拍摄）少一截，老板承认这是事实且达不成一致，但表示拍摄的不会比后期少，已掌握平衡；这是老板唯一愿意解释的发放原因，其他奖项发放属老板主观意志、不谈判。
+- **员工自我评价未达预期**：张启自评 2023 年未达到自己的预期，原因包括效率、时间，以及项目上对同事和甲方的沟通做得不太好，明年继续改进。
 # 改进计划
-- **针对成本控制差**：老板承认成本控制是公司最大问题，根源在于老板对成本关心关注不够、不够雷厉风行、出现问题未及时解决，明年开会时再讨论成本控制的具体方案。
-- **针对短视频账号未变现**：老板表示明年期待账号开始变现，作为老板会投入更大精力做这件事，给予足够重视。
-- **针对执行部门加班多、休息时间被侵占**：老板期待明年更多进行组织协调，提高效率，尽可能少侵占大家休息时间。
-- **针对商务部门支持不足**：老板承认今年对商务部门给予的支持、管理或关心不够，明年会反思这个问题，并考虑给商务人员更多支持和帮助（如张启，老板表示后面会考虑帮他聊项目、打理事务）。
-- **针对拍摄外援成本高**：员工钱德峰建议尝试让公司内部人员参与拍摄（如按机位、保证机器不关机），一方面提升收入，另一方面体验拍摄工作；老板回应期待明年大家都能参与拍摄，起码能应付得了，对个人市场价值也是提升。
-- **针对加班多、人员不足**：老板承认加班多的最直观因素是人员不够，本质上是老板没有及时招合适或足够人数的人员，属于判断失误。
-- **针对后期人员技术水平提升空间**：老板对刘腾宇提出更高期待，希望综合后期技术水平更高，能完美胜任各种类型；对市井期待能解决一部分公司认为比较难的问题。
-- **针对沟通能力提升**：老板对欧阳提出沟通能力需再爬坡的期待；对李国宇提出沟通能力提升的期待。
-- **针对拍摄人员执行能力**：老板对钱德峰提出更高期待，希望有更强的执行能力，包括项目或沟通谈判方面。
-- **针对员工参与拍摄的配合度**：老板强调明年靠这个方向靠，希望大家每个人都能参与拍摄；被领导问到拍摄安排时，不能直接说没空，应解释手头忙的事务或勉为其难安排一下，直接说没空是非常不职业的。
-- **针对年终奖额度问题**：老板表示年终奖具体额度明年开会时再讨论。</t>
+- **针对成本控制差（利润率仅24%或27%，成本支出390万元）**：老板明确表示成本控制问题**明年开会时再讨论**，未给出具体方案。
+- **针对年终奖额度问题**：老板表示年终奖额度问题**明年开会时再讨论**，未给出具体调整方向。
+- **针对账号未变现（变现评分7.5分，重点项目未完成）**：老板表示明年将**投入更大精力**推动账号开始变现，并给予足够重视。
+- **针对拍摄人员不足、外援成本高**：老板表示明年将**鼓励全员参与拍摄**，希望每个人都能应付基本拍摄，以降低外援依赖；同时强调员工被安排拍摄时不应直接说“没空”，应说明手头工作或勉为其难安排，否则属不职业表现。
+- **针对加班多、人不够（后半年基本都在加班）**：老板承认是**判断失误**，本质是未及时招到合适或足够数量的人员，明年将反思并改进人员配置。
+- **针对老板对商务部门支持不够（实打实项目约300万）**：老板表示明年将**反思管理、关心与支持不足的问题**，并考虑给商务部门更多支持和帮助。
+- **针对老板对执行部门组织协调不足（项目密集、侵占休息时间）**：老板表示明年将**更多进行组织协调**，提高效率、减少侵占员工休息时间。
+- **针对拍摄技术达不到段位（部分外援因技术水平达不到而使用）**：老板期待李国宇等拍摄人员能达到更高段位，向段位高的人多学习，以承接部分原本外包的高难度拍摄。
+- **针对后期综合技术水平提升空间**：老板对刘腾宇提出更高期待，希望其**综合后期技术水平更高**，能完美胜任各种类型工作。
+- **针对沟通能力需提升**：老板对欧阳提出期待，希望其**沟通能力再爬坡**；对李国宇也提出沟通能力提升的期待。
+- **针对员工参与拍摄意愿不足**：员工钱德峰建议公司内部人员可尝试参与简单拍摄（如按个机位、保证机器不关机），以降低外援成本，老板表示明年将**往这个方向靠**，鼓励全员参与。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>86.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/5953</t>
+          <t>24562/6435</t>
         </is>
       </c>
     </row>
@@ -2066,84 +2075,81 @@
       <c r="C5" t="inlineStr">
         <is>
           <t># 全文摘要
-本次专项讨论会由办事处领导刘主任主持，召集小区业委会成员（邱主任、王艳芳、李艳南等）与物业经理吴经理，就小区服务质量、物业费欠缴、业主大会召开及物业起诉等矛盾进行协调。会议围绕业主大会召开与表决、小区问题清单及物业回应、物业起诉与法律程序、物业费与服务质量矛盾四方面展开，双方对立严重，未达成实质共识。
-业委会方面提出业主自发接龙有200多户参与，主张召开业主大会表决是否更换物业，并列举小区10条问题：入户门柱灯从未开启、内部水系与迎宾水系从未开启、监控几乎全部损坏（上月进贼未获取数据）、监控室24小时值班服务自王艳芳上任后荒废、绿化维护不力（去年死树多棵，门口死三棵）、北边围墙用烂铁皮遮挡且有缺口、物业承诺定制围挡未安装、快递柜/直饮水机/宽带/暖气开户等民生问题无进展、雨水倒灌自2019年存在未解决、物业人员从办公室近10人减至4人、维修从5人减至2人。
-物业经理吴经理逐一回应：门柱灯因能耗成本无法运营；水系存在严重质量问题属地产配套未完成；监控损坏因无费用（物业费欠账170多万，回款仅40万，人工成本年超100万）；围墙属红线外且涉及违建，费用高未安装；民生问题属地产前期配套；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结。物业指责业委会煽动业主不缴费，称已掌握证据，宣布本月将正式起诉业委会，理由包括选举违法、煽动业主、阻碍经营等，并称已与滨城区人民法院和高级人民法院沟通，欠费超一年业主不能成为业主代表。业委会成员表示将反诉并拿出证据，质疑物业窥探业主隐私。业委会认为物业服务没有滞后性，不能先收钱再服务，提出可能集体起诉要求返还部分物业费；物业称欠费导致无钱维修，形成恶性循环。会议无实质结果，业委会决定正常推进业主大会，物业表示将起诉。
+本次专项讨论会由社区领导刘主任主持，召集物业经理吴经理、业委会成员邱主任及业主代表等，就小区服务质量、物业费欠费、法律诉讼及业主大会召开等矛盾进行协调。业委会提出业主自发接龙有200多户要求召开业主大会表决物业去留，物业方则宣布已与集团法务沟通，将于本月正式起诉业委会及业主代表，双方未达成一致。业委会成员列举小区10条问题，包括入户门柱灯从未开启、内部水系及迎宾水系从未开启、监控几乎全部损坏（上个月进贼无监控数据）、监控室24小时值班荒废、绿化维护差（去年死树多）、北边围墙用烂铁皮且有缺口、民生配套（快递柜、直饮水、宽带、暖气）无进展、雨水倒灌严重（2019年起有财产损失）、物业人员从办公室10人减至4人、维修从5人减至2人。物业经理逐条回应，称部分问题属地产责任或费用不足，双方就责任归属激烈争论。物业称业主欠费170多万，回款40万即可解决部分问题；园区保护收入100来万，人工成本100多万，每年亏损，维修费今年花了几十万。业委会成员质疑物业服务无滞后性，不能先收钱再服务。物业称欠费人员不能成为业主代表。
+物业宣布已与集团法务沟通，本月正式起诉业委会及业主代表，称掌握业主群内煽动证据，已与滨城区人民法院、高级人民法院沟通。业主代表表示将反诉，要求物业拿出证据，并质疑物业窥探业主隐私。业委会决定正常推进业主大会，不再与物业调解；物业表示将走法律程序。社区领导建议双方冷静，但业委会认为矛盾不可调和，坚持推进业主大会。
 # 分段速览
-## 00:10-05:37 开场与背景铺垫
-会议开场，发言者提及装备、工资、群体比例等零散话题，随后转向小区供暖开户费问题。发言者2指出园区从建设至今从未验收，开户费应由地产出资并交接管道给供暖公司，但至今未完工，导致业主误以为是物业责任。发言者3确认费用已交清，发言者2补充开发商已交配套费但去向不明，涉及金额约9亿。发言者4提到业主买房满怀希望不愿退房，发言者2表示二期补助约29%，但推进受阻。
-## 05:49-10:05 业主缴费与接龙情况
-发言者4说明业主自发组织接龙，约200多户参与，主要议题是召开业主大会。发言者2提到业主自发组织缴费，涉及400元费用，二期三期合计约20来户交费。发言者2强调物业费欠账问题，称50户目标仅达到10户，达不到则无法提供服务。发言者4表示自家暖气管道少，部分业主担心管道问题影响明年供暖。
-## 10:14-15:42 会议目的与程序讨论
-发言者2强调会议目的是坦诚相待、共同商量，不暴露敌对情绪，成立业主委员会需大家共事。发言者4建议尽快召开业主大会，由全体业主表决是否更换物业，强调业委会无权单方面决定。发言者2质疑接龙程序，认为讨论应有结果，不能失控。发言者5补充接龙业主心声：要求整改小区问题，若整改不了可招标换物业，原物业也可参与投标。
-## 15:51-21:23 物业方表态与起诉声明
-发言者2代表物业方郑重声明：事先未接到业主大会沟通，质疑接龙有组织性。物业已与集团法务沟通，本月将正式起诉业委会，理由是选举违法、后期决策违规、在业主群煽动等。发言者2称已与滨城区人民法院和高级人民法院沟通，掌握业主群证据，欠费超一年者不能成为业主代表，起诉可能影响个人经营。
-## 21:34-30:53 业委会列举小区十大问题
-发言者4逐条列举小区问题：①入户门柱灯从未开启；②内部水系从未开启；③迎宾水系从未开启；④监控几乎全部损坏，上月进贼未获取数据；⑤监控室24小时值班服务自王艳芳上任后荒废；⑥绿化维护不力，去年死树多棵；⑦北边围墙用烂铁皮遮挡且有缺口，社会人员可随意进出；⑧快递柜、直饮水机、宽带、暖气开户等民生问题无进展；⑨雨水倒灌自2019年存在，造成财产损失；⑩物业人员从办公室近10人减至4人，维修从5人减至2人。
-## 31:22-38:01 物业方逐条回应
-发言者2回应：门柱灯因能耗成本无法运营，业委会曾承诺全员缴费后修复；水系存在严重质量问题，属地产配套未完成；监控损坏因无费用，物业费欠账170多万、回款仅40万，人工成本年超100万；监控画面已第一时间提供给刑警；绿化死亡因业委会10月成立后已入冬季；北边围墙属红线外且涉及违建，费用高未安装；民生问题属地产前期配套；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结。
-## 38:53-46:14 双方激烈交锋
-发言者4反驳物业服务不应有滞后性，不能先收钱再服务，问题从交房至今一直存在。发言者2坚持走法律程序，称起诉期间无法换物业。发言者4表示业委会成立之日即自动解除物业合同关系，双方就法律程序争执不下。发言者4称99%业主支持换物业，仅代表个人意见，并指责物业经理说话欠妥，如进贼时反问"你交物业费了吗"。
-## 46:50-53:01 矛盾激化与调解尝试
-发言者3指出恶性循环：服务不好→业主不缴费→物业无钱整改→服务更差，称区领导、市领导也难以解决。发言者4提出可能集体起诉要求返还部分物业费。发言者8质疑物业窥探业主隐私，表示将反诉。发言者5主张业主大会开与不开都应推进，需与物业打招呼明确议题。发言者3建议双方冷静，往好的方向发展。
-## 53:14-01:03:16 调解失败与会议结束
-发言者8澄清被造谣与物业有关，愿公开查证。发言者3建议物业反思历史累积问题，拿出真实行动赢得业主信任。发言者7称物业入不敷出，欠费170多万，回款仅40万，今年亏损拉大。发言者3反问物业为何不能把地产公司签回来解决问题，发言者7称地产已申请破产。双方均表示难以调和，业委会决定正常推进业主大会，物业表示将起诉，会议无实质结果。
+## 00:10-05:02 开场与背景铺垫
+会议开场，发言者1与发言者2简短交流装备与生活话题。发言者2随后谈及公司管理、人员规模（提及10,200人目标）及项目推进情况，内容零散且缺乏明确主线。其间穿插关于供暖开户费、地产配套费缴纳情况的讨论，发言者2称相关费用已全部缴纳，但涉及开发商与供暖公司交接的流程尚未完成，园区至今未验收，导致责任归属不清。
+## 05:02-10:05 业主诉求与物业矛盾初现
+发言者2继续讨论物业费收缴与业主配合问题，提及二期补助比例约29%、业主自发组织缴费（约400元/户）等细节。发言者4指出业主买房满怀希望、不愿退房退费。发言者2强调成立业主委员会需坦诚相待、避免对立情绪，并提及配电室三级管理、业主群数量（工作群1个、准业主群5个）等事项。发言者5补充筹备组6人各联系一部分业主的情况。
+## 10:05-15:42 业主大会动议与程序讨论
+发言者4介绍业主自发接龙已有200来户参与，主要议题是召开业主大会表决物业去留，并明确业委会无权单方面撤换物业。发言者2质疑接龙程序合法性，认为讨论需有明确结果而非空谈。发言者5总结接龙业主心声：一是要求整改小区问题，二是若整改无效可重新招标物业（原物业也可参与投标）。双方就召开业主大会的程序、表决方式展开初步交锋。
+## 15:42-21:23 物业宣布起诉与程序争议
+发言者2代表物业方正式表态：事先未接到业委会沟通，质疑接龙有组织性；宣布因业委会成立及工作过程中存在违法情况，已与集团法务沟通，将于本月正式起诉业委会及业主代表。发言者2称已掌握业主群内证据，并提及欠费超一年人员不能成为业主代表。发言者4则坚持业主大会应正常推进，双方在诉讼期间能否召开业主大会的问题上产生分歧。
+## 21:23-31:22 业委会列举十大问题
+发言者4系统列举小区10条问题：入户门柱灯从未开启、内部水系与迎宾水系从未开启、监控几乎全部损坏（上个月进贼无监控数据）、监控室24小时值班荒废、绿化维护差（去年死树多）、北边围墙用烂铁皮且有缺口、民生配套（快递柜、直饮水、宽带、暖气）无进展、雨水倒灌严重（2019年起有财产损失）、物业人员从办公室10人减至4人、维修从5人减至2人。发言者2多次打断要求其停止发言，但发言者4坚持陈述完毕。
+## 31:22-38:53 物业逐条回应与经营困境
+发言者2逐条回应：门柱灯因能耗成本过高无法运营；水系存在质量问题属地产维修责任；监控维修因费用超运营承担，园区保护收入100来万而人工成本100多万，每年亏损；绿化死亡因冬季无法更换；北边围墙属红线外且涉及违建；民生配套属地产前期配套；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结。发言者7补充称业主欠费170多万，回款40万即可解决部分问题。
+## 38:53-46:14 矛盾激化与调解失败
+发言者4反驳物业服务无滞后性，不能先收钱再服务，并指出门柱灯、水系、监控等问题从交房起就存在，非物业近期亏损所致。发言者2坚持已走法律程序，称业委会成员在业主群煽动不缴费。发言者4表示已无调解必要，主张直接表决换物业。发言者2回应称起诉期间无法换物业，且前提是结清费用。双方在围栏定制、半热带安装等具体事项上再次争执，矛盾进一步激化。
+## 46:14-53:01 欠费循环与反诉表态
+发言者3指出问题陷入死循环：服务不整改→业主不缴费→物业没钱→服务更差。发言者4提出业主可能集体起诉要求返还部分物业费。发言者7确认已与集团法务沟通，今日操作起诉手续，并称已截屏业主群动态作为证据。发言者8质疑物业窥探业主隐私，表示将反诉并要求对方拿出证据。发言者4还指控物业经理曾对业主说「不交物业费就上你家吃饭」，发言者7要求其拿出录音。
+## 53:01-01:03:16 社区调解与最终表态
+发言者3（社区领导）建议双方冷静，指出矛盾系历史多方面原因累积，物业需反思服务，业主也应体谅物业难处。发言者7重申物业入不敷出、业主欠费170多万，称地产公司已申请破产，无法追讨配套问题。发言者4表示业委会将正常推进业主大会，不再与物业调解。发言者2总结会议未解决实质问题，双方隔阂加深。最终业委会决定推进业主大会，物业表示将走法律程序，会议无果而终。
 # 要点梳理
 ## 业主大会召开与表决
-- **业主接龙**：业主自发组织接龙，约200多户业主参与，主要议题为召开业主大会。
-- **业委会主张**：业委会成员邱主任提出，业委会或业主无权决定撤换物业，须由业主大会表决，建议尽快召开业主大会让全体业主表决。
-- **工作群情况**：业委会工作组仅1个群，准业主分5个群，共6个群；筹备组成立时6人，每人联系一部分业主。
-- **接龙群来源**：接龙群为最早业主自发组织的业主群，由老邱哥建群，从交房起已有5、6年。
-- **物业质疑**：物业经理吴经理称未接到任何关于召开业主大会的沟通，质疑接龙有组织，议题不明。
-- **表决方式**：吴经理称会议以表决为主，需5个群业主同意；业委会成员表示诉讼期间若无法律规定，业主大会应照常召开。
-- **业委会决定**：业委会决定正常推进业主大会，表决是否更换物业。
-## 小区问题清单及物业回应
-- **门柱灯**：业委会成员指出入户庭院门柱灯从未开启；物业称因园区能耗成本无法运营，曾与业委会沟通，业委会承诺全员缴费后拿出部分费用修复。
-- **内部水系与迎宾水系**：内部水系自卖房后从未开启，迎宾水系作为小区门脸也从未开启；物业称水系从交付起存在严重质量问题，泵无法运转，属地产配套未完成，由地产维修。
-- **监控损坏**：监控几乎全部损坏，上月小区进贼，110派出所及刑警大队未从监控获得数据；物业称监控损坏因无费用，超出运营承担。
-- **监控室值班**：监控室交房时配备24小时值班，门铃有一键直达功能；业委会称自王艳芳上任后服务荒废，无人值班。
-- **绿化维护**：去年死树多棵，小区门口死三棵；业委会成员曾致电物业管家反映树生病，管家称经理说等明年看能否发芽；物业称业委会10月成立备案，之后为冬季，换树责任难定。
-- **北边围墙**：北边用烂铁皮遮挡，最西边有缺口，社会人员可随意进出；业委会责令整改后物业拆除铁皮但未装新围挡，被指哄骗业主已定制；物业称围墙属红线外、涉及违建，不在物业服务范围，曾协调厂家定做但因费用高未成，费用由物业承担，与业委会沟通不下5次。
-- **民生配套**：快递柜、直饮水机、宽带覆盖、暖气开户等无进展，由业委会全程办理；物业称属地产前期配套，若开通费用由业主承担。
-- **雨水倒灌**：自2019年起存在，业主有财产损失，多次反映无进展；物业称园区地势四周高中间矮，车库设计为斜坡向下，属地产设计建设问题，超出排水承载范围。
-- **人员配备**：物业办公室从近10人减至4人，维修从5人减至2人；物业称地产曾给补亏款但未结账，现项目20来人，年人工成本100多万。
-- **物业收支**：物业称园区保护收入约100万，人工成本超100万，不含垃圾清运费、能耗、维修、税费等，每年亏损，可公开查账。
-## 物业起诉与法律程序
-- **起诉决定**：物业经理吴经理宣布已与集团法务沟通，本月将正式起诉业委会，理由包括选举违法、煽动业主、阻碍经营。
-- **法院沟通**：物业称上午9:52与高级人民法院通电话，也与滨城区人民法院沟通，均有记录。
-- **证据掌握**：物业称已掌握业主群煽动不缴费记录，很多业主已反馈并截屏保存。
-- **欠费限制**：物业称欠费超过一年的业主不能成为业主代表，顶名也不能，将依法追究责任。
-- **业委会回应**：业委会成员表示将反诉并拿出证据，质疑物业窥探业主隐私。
-- **起诉影响**：物业称起诉期间可能无法换物业公司；业委会称若法律无此规定，业主大会应照常召开。
-## 物业费与服务质量矛盾
-- **服务滞后性**：业委会认为物业服务没有滞后性，全滨州小区没有先收钱再服务的先例。
-- **欠费情况**：物业称业主欠物业费170多万，回款仅40万，账上一分钱没有，无法解决维修问题。
-- **恶性循环**：业委会称服务不好业主不愿缴费，物业称欠费导致无钱维修，双方争执不下。
-- **集体起诉提议**：业委会成员提出在最终解决前，可能集体起诉要求返还部分物业费。
-- **物业经理言论**：业委会称物业经理曾对业主说"不交物业费就上你家吃饭"，物业经理否认并要求拿出录音。
+- **业主接龙**：业主自发组织接龙，约200余户业主参与，主要议题为召开业主大会，表决物业去留。
+- **业委会主张**：业委会成员邱主任提出，业委会或业主无权单方撤换物业，须由业主大会表决；建议尽快召开业主大会，由全体业主决定。
+- **物业质疑程序**：物业经理吴经理称，召开业主大会前须事先与物业沟通，但物业未接到任何通知，也未参与议题组织。
+- **表决与讨论定位**：吴经理称会议最终结论以表决为主，但需先讨论小区问题能否整改；业委会成员认为讨论已无必要，直接表决即可。
+- **诉讼期间能否开会**：吴经理称起诉期间业主无法行使表决权；业委会成员表示若法律无禁止条款，业主大会照常推进。
+- **业委会立场**：业委会成员称成立业委会即自动解除与物业的合同关系；物业方不认可此说法，双方未达成一致。
+- **社区调解**：社区领导刘主任建议双方冷静沟通、互相体谅，但业委会成员认为矛盾已不可调和，坚持推进业主大会。
+## 小区问题清单与物业回应
+- **入户门柱灯**：业委会成员称每户庭院门柱灯从未开启；物业称因园区能耗成本过高、物业已无力承担，曾与业委会沟通并承诺收费后修复。
+- **内部水系与迎宾水系**：业委会称水系自交房以来从未开启，业主加价购买水系旁房产；物业称水系泵存在严重质量问题，属地产配套未完成，应由地产维修，非物业责任。
+- **监控损坏**：业委会称监控几乎全部损坏，上个月小区进贼，110派出所及刑警大队均未从监控获得数据；物业称已第一时间将监控画面截取给派出所和刑警，并出示刑警调取监控的照片记录。
+- **监控室值班**：业委会称交房时监控室应24小时有人值班，门铃有一键直达功能，但王艳芳上任后该服务荒废；物业未正面回应。
+- **绿化维护**：业委会称去年死树多，小区门口两侧已知死3棵，业主报修后物业管家称「经理说了，明年看能不能发芽」；物业称业委会10月成立备案，此后为冬季，无法更换，更换后死亡责任难定。
+- **北边围墙**：业委会称北边长期用烂铁皮遮挡，最西边有缺口，社会人员可随意进出；物业称该处属红线以外、涉及违建官司，不在物业服务范围内，曾协调厂家定做但因费用过高未成，费用本应由物业承担，已与业委会沟通不下5次。
+- **民生配套**：业委会称快递柜、直饮水、宽带覆盖、暖气开户等多年无进展，均由业委会全程办理；物业称按建设条例和前期配套要求，属地产前期配套，后期开通费用由业主承担。
+- **雨水倒灌**：业委会称2019年起每户均有不同程度财产损失，多次反映无解决方案；物业称园区地势四周高中间低、车库设计为斜坡向下，属地产前期设计建设问题，超出物业解决范围。
+- **人员配备**：业委会称物业办公室从近10人减至4人（含经理），维修从5人减至2人；物业称因地产欠补亏款未结，现项目20来人，年人工成本100多万。
+## 物业费欠费与经营状况
+- **欠费金额**：物业称业主欠物业费170多万，回款40万即可解决部分维修问题；业委会成员在群内号召不缴费，物业称有记录并已交法院。
+- **收支状况**：物业称园区保护收入100来万，人工成本100多万，另含垃圾清运费、能耗、维修、税费及办公成本，每年亏损，账目可公开查证。
+- **维修支出**：物业称今年维修费已花几十万。
+- **服务与收费顺序**：业委会成员称物业服务无滞后性，全滨州小区无先收钱再服务之理；物业称欠费人员不能成为业主代表，顶名亦不可。
+- **缴费与整改循环**：社区领导指出业主因整改未落实不愿缴费、物业无钱整改的恶性循环，区领导或市领导也难以解决。
+## 法律诉讼与反诉
+- **物业起诉决定**：物业称今天上午已与集团法务沟通，本月将正式起诉业委会及业主代表，理由包括选举违法、决策违规、群内煽动、阻碍经营造成经济损失。
+- **法院沟通**：物业称上午9:52与高级人民法院通话，并与滨城区人民法院沟通，均有沟通记录。
+- **证据收集**：物业称已在业主群掌握大量证据并截屏存档，业主动态已有多名业主反馈。
+- **业主反诉**：业主代表称只要物业起诉就反诉，要求物业拿出证据；并质疑物业窥探业主隐私。
+- **欠费与代表资格**：物业称欠费超一年人员不能成为业主代表，将依法追究责任。
 ## 结论与决定
-- **业委会决定**：正常推进业主大会，表决是否更换物业。
-- **物业决定**：本月正式起诉业委会，理由为选举违法、煽动业主、阻碍经营。
-- **会议基调**：办事处领导刘主任建议双方冷静沟通、物业拿出真实行动，但双方均表示难以调和。
+- **业委会决定**：正常推进业主大会，不再与物业调解；业委会成员称只要业主同意换物业，物业可起诉，业委会按流程推进。
+- **物业决定**：本月正式起诉业委会及业主代表，称起诉期间业主无法行使表决权；物业称前提是费用结清。
+- **未达成一致**：业主大会能否在诉讼期间召开、小区问题整改责任归属（物业/地产）、物业费欠费回款40万能否落实，均未达成一致。
 ## 行动项与分工
-- **业委会**：正常推进业主大会召开，组织业主表决是否更换物业。
-- **物业**：本月内完成对业委会的起诉，收集业主群煽动不缴费等证据，与集团法务及法院沟通。
-- **办事处**：刘主任负责协调双方矛盾，建议物业拿出真实行动改善服务。
+- **物业**：本月内正式起诉业委会及业主代表，已与集团法务及法院沟通，将提交业主群内证据。
+- **业委会**：正常推进业主大会召开，不再与物业调解；业主代表称将反诉并准备证据。
+- **社区领导**：刘主任建议双方冷静沟通，但未形成具体跟进安排。
 ## 待确认与风险
-- **业主大会合法性**：业主大会是否能在物业起诉期间召开，双方存在分歧。
-- **物业费与服务顺序**：物业费缴纳与服务改善的先后顺序未达成一致。
-- **责任归属**：小区问题整改责任归属（物业还是地产）未明确。
-- **安全风险**：监控几乎全部损坏、北边围墙有缺口，社会人员可随意进出，上月进贼未获取数据。
-- **运营风险**：物业费欠账170多万，回款仅40万，物业运营困难，今年亏损额度拉大。
-- **雨水倒灌风险**：问题未解决，明年大雨可能再淹。</t>
+- **业主大会合法性**：诉讼期间能否召开业主大会未确认，双方各执一词。
+- **监控安全隐患**：监控几乎全部损坏，上个月进贼无监控数据，存在安全风险。
+- **围墙缺口风险**：北边围墙缺口，社会人员可随意进出，业主担心过年安全。
+- **雨水倒灌风险**：问题未解决，明年大雨可能再淹。
+- **人员配备不足**：物业办公室4人、维修2人，影响服务质量。
+- **矛盾激化风险**：物业与业主矛盾激化，社区领导称隔阂越来越深，可能影响小区稳定。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>73.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/4692</t>
+          <t>21511/4765</t>
         </is>
       </c>
     </row>
@@ -2392,45 +2398,49 @@
       <c r="C6" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌论坛由一位主持人（代表多模态大模型与具身智能融合方向）组织发起，邀请多位老师与博士生围绕具身智能领域的关键技术路线与产业前景展开研讨。参与方包括穆老师（机械与传感器方向）、王岳老师（强化学习方向）、赵昊老师（计算机视觉方向）、杨立新老师（真机数据采集）、李欣老师、静波老师、业界嘉宾，以及雄辉、薛寒、志龙等博士生，分别来自强化学习、柔性物体操作、具身世界模型等方向。研讨旨在碰撞不同流派观点，探讨具身智能从技术路线到产业落地的核心问题。讨论覆盖大模型架构与硬件形态、世界模型定义与构建、强化学习与模仿学习路线之争、数据采集与仿真数据、国产仿真系统等五个议题，确认了软硬件协同、混合策略学习等观点，并遗留了世界模型统一性、国产仿真系统等未决问题。
-- **具身智能大模型架构与硬件形态**：探讨大模型应采用端到端还是分层架构，以及具身智能的最终形态是人形还是特种机器人，涉及软硬件协同优化与产业前景判断。
-- **世界模型的定义与构建**：讨论强化学习与计算机视觉两个领域对世界模型的不同理解，核心分歧在于是否需要3D表征与物理规律建模，以及世界模型能否统一。
-- **强化学习与模仿学习的路线之争**：分析两大策略学习流派各自的局限，探讨先模仿后强化、混合策略等可行路线，以及真机场景下reward的获取问题。
-- **数据采集与仿真数据**：比较真机遥操数据、仿真生成数据与互联网视频数据三种数据来源的质量与成本，讨论如何规模化采集高质量数据。
-- **国产仿真系统**：讨论中国是否强依赖英伟达生态，以及国产仿真系统能否出现并支撑具身智能发展。
+本次圆桌论坛以「具身智能」为主题，由穆老师主持，汇聚了来自学术界与产业界的多位学者、博士生及嘉宾，包括于洋老师、卢策武老师、赵昊老师、王岳老师、杨立新老师、李欣老师、静波老师，以及雄辉、薛寒、志龙等博士生。研讨围绕具身智能的形态与硬件、世界模型、策略学习路线、数据采集等核心议题展开，旨在通过跨方向（多模态大模型、强化学习、具身模型、机械与传感器、产业投资）的思想碰撞，探讨具身智能发展的关键问题与未来路径。与会者观点纷呈，讨论热烈，未形成统一结论。
+- **具身智能的形态与硬件期待**：探讨具身智能最终收敛为何种形态（人形机器人或特种机器人），以及现有硬件（如工业机械臂）在寿命、可靠性、柔顺性上能否支撑大规模真机评估与数据采集。
+- **世界模型的定义与是否需要3D归纳偏置**：围绕强化学习领域与计算机视觉领域对世界模型的不同理解展开，核心争议在于世界模型是否必须可交互、是否需要引入3D/物理规律等归纳偏置，以及一个统一的世界模型能否同时建模不同物理环境的dynamics。
+- **强化学习与模仿学习的路线之争**：讨论在数据规模与仿真环境受限的现状下，策略学习最终应依赖模仿学习、强化学习还是两者融合（如先模仿预训练再强化微调），以及真机场景下reward的获取难题。
+- **数据采集与质量**：对比真机遥操数据与仿真生成数据两条路线，探讨如何保证数据质量（视角、标定、物体运动信息）、如何低成本规模化采集（可穿戴设备、脑机接口），以及仿真数据与真实数据结合使用的效果。
+- **仿真系统的国产化**：讨论中国具身智能仿真是否强依赖英伟达生态，以及国产仿真系统（如宋应团队）能否在脱钩风险下实现替代。
 # 核心观点
-- **大模型架构与硬件形态**：主持人提出端到端模型与分层模型之争，以派灵收集6000多小时数据训练端到端模型为例；穆老师从机械角度反问具身形态收敛方向，举例星际穿越中的变形机器人；王岳老师认为大模型不应完全端到端，至少应分两层，大脑不变、小脑自适应肢体，以手断后大脑仍能工作为例；赵昊老师从产业角度分析，认为具身智能是手机和汽车之后的第三个万亿级市场，融资将经历四波，分别对应自动驾驶、大模型、互联网的规模，并提到马斯克公司花一半精力做灵巧手，实现22自由度，车厂和微电子制造厂已有97%以上自动化使用机械臂。结论是人形机器人和特种机器人将来都会存在。
-- **世界模型定义与构建**：志龙从强化学习角度阐述世界模型的可交互性，可追溯到1990-1991年Sutton的Dyna-Q文章，2018年Schmidhuber和LeCun定义包含表征和转移两个组件；赵昊老师从CV角度强调三维重建，认为CV界追求重建物理世界可作为RL世界模型的工具，并提到UniSim需要3D inductive bias，梦想写一篇data bias trade off的paper；王岳老师举例刺客信条游戏与真实世界跳楼的不同结局，认为世界模型无法同时建模两个dynamics，可能做不到统一，但policy有可能统一；薛寒博士提出不同物理结构可以有统一表征，王岳老师认为需要加condition，工程难度高。结论是世界模型在RL和CV界关注点不同，是否需要3D inductive bias由数据决定。
-- **强化学习与模仿学习路线之争**：业界嘉宾分享公司采用模型强化加机理融合的方式，认为监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境，sim-to-real迁移困难，其强化PC工作考虑任务分层，上层强化学习，底层用MPC或DWA等传统方法；薛寒博士认为复杂任务应先模仿后强化，单独模仿或单独强化都不行，举例AlphaStar和GPT都是先模仿后强化；王岳老师认为PID有反馈，可作为强化学习的reward；李欣老师认为模仿学习和强化学习并不冲突，只是获取运动先验的不同方式。结论是当前阶段应采用混合方式，先模仿后强化是实际可行的路线。
-- **数据采集与仿真数据**：杨立新老师提到Open X数据集相机视角不固定，影响模型表现，强调标定重要，手眼标定问题至今未完全解决，Open X数据集缺少物体运动信息，orkin从采集时记录物体运动；薛寒博士提到柔性体操作如叠衣服、系鞋带等任务仿真困难，UCLA蒋正凡老师做过高性能仿真技术，认为reward数据是低成本方案，现实生活是最好的仿真器，派灵收集1万小时数据但离GPT-3级别还远，终极数据采集形态是脑机接口或机电方式，互联网视频数据与机器人所需数据不同，例如叠衣服视频都是平铺状态；主持人提到自己洗ego4d数据集洗了三个月，仿真数据加少量真机数据可显著提升成功率，例如300条仿真数据加20条真机数据；赵昊老师认为真实数据还是仿真数据要看成本，case by case。结论是仿真数据与真实数据结合是有效方案，未来应重视无标注数据。
-- **国产仿真系统**：主持人提到Isaac Sim/Isaac Lab开放了柔性物体仿真接口，是目前最好用的；赵昊老师提到朋友宋应赌国产替代，认为会被卡脖子，技术上会统一，但business上复杂。
+- **具身形态与硬件期待**：穆老师提出具身智能最终形态是像人形机器人还是科幻片中可变形机器人，并提及机械领域的机械智能（软手抓取、摩擦顺应性）。薛寒博士指出硬件需高寿命和高可靠性，现有工业机械臂不适合大规模真机评估，需个人柔顺硬件结构支持scale up的evaluation。穆老师补充软硬件协同优化观点，提到松龄产品第二代在遥操和策略部署上优于第一代，与任老师合作的凝胶夹爪可反馈触觉且更稳。王岳老师认为大模型不应从上到下贯穿，硬件变化时底层控制需自适应，以人手断后大脑仍能工作为例，主张大脑不变、小脑adaptive到肢体。赵昊老师从第一性原理出发，认为人形机器人和特种机器人都会存在，人形机器人会有灵巧手，提到马斯克公司花一半精力做22自由度灵巧手。
+- **世界模型定义与3D归纳偏置**：志龙从强化学习角度提出世界模型第一要素是可交互，概念可追溯到1990-91年Sutton的Dyna-Q文章，强调表征与转移两个组件。赵昊老师认为CV界追求重建物理世界，可作为RL中world models的工具，但当前三维计算机视觉技术栈深，RL博士生难以完全学习，导致学术界不关注三维表征。赵昊老师提出数据与归纳偏置的权衡观点，梦想写一篇data bias trade off论文，认为数据多时需要的归纳偏置少，数据少时需要的多，并以ImageNet、GPT成功说明不需要inductive bias，UniSim则需要3D归纳偏置。王岳老师提出世界模型可能无法统一，因为存在歧义问题（游戏与物理世界相同观测不同结局），而policy可能统一，认为一个世界模型无法同时建模不同dynamics。薛寒博士认为强化学习的world model是任务导向的，CV的world model可能不必要，目标是更好学策略，不一定要有action。
+- **强化学习与模仿学习路线**：杨立新老师介绍公司采用模型强化加机理融合方式，认为监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境，sim-to-real迁移困难，需限制决策空间和任务设定，上层用强化学习做决策，底层用MPC或DWA等传统方法执行。薛寒博士认为复杂任务应先模仿后强化，单独模仿或强化都不行，以AlphaStar和GPT为例说明先模仿提供先验信息可降低样本复杂度，但人类行为不一定最优时需强化优化。王岳老师提出PID有反馈，可作为强化学习的reward，认为所有PID能做的系统必然有反馈，强化必然走得成。李欣老师认为强化学习和模仿学习并不冲突，只是想要运动先验，有数据可用模仿学习，无数据可用强化学习获取，再通过RL完成任务。
+- **数据采集与质量**：杨立新老师提到Open X数据集相机视角无法固定，影响模型表现，强调标定非常重要，手眼标定问题至今解决得不好，orkin从采集数据角度出发记录物体运动，不只有本体信息。薛寒博士提到柔性体操作任务如叠衣服、系鞋带，现有仿真技术难以模拟，需IPC等先进图形学技术但算力要求高，认为reward数据是低成本方案，现实生活是最好的仿真器，终极形态是脑机接口或机电方式，现阶段可穿戴设备是能scale的方案，互联网视频数据与机器人所需数据不同（叠衣服视频是平的状态，机器人需处理混乱状态）。穆老师提到自己洗ego4d数据集洗了三个月，互联网数据质量低，仿真数据300条加上20条真机数据成功率显著提升，仿真数据可覆盖物体随机位置和初始状态。赵昊老师提出2025年应推广大规模利用无标注数据，如segment anything和depth anything，认为真实数据与仿真数据比例讨论已过时，应加入无标注真实数据作为第三domain。
 # 达成共识与解决方案
-- **软硬件协同优化**：主持人（多模态大模型与具身智能融合方向）与王岳老师一致认为，具身智能是软硬件协同进化的范式，依据是松灵机器人两代产品在遥操与策略部署上的代际提升，以及加凝胶夹爪在触觉反馈与摩擦力上的改进。**结论：具身智能必须走软硬件协同优化路线**。
-- **大模型分层架构**：王岳老师提出大模型不应从上到下完全端到端，至少应分两层——大脑不变、小脑自适应肢体，依据是手断后大脑仍能工作、底层控制需适配新动力学的类比；主持人对此表示认可。**结论：端到端模型与分层模型并非互斥，分层架构更利于硬件迭代**。
-- **人形与特种机器人并存**：穆老师提出具身形态收敛问题后，赵昊老师从产业角度分析，认为人形机器人（如马斯克公司投入一半精力研发的22自由度灵巧手）与特种机器人（如车厂、微电子制造厂中已实现97%以上自动化的机械臂）将来都会存在。**结论：人形机器人和特种机器人将长期并存**。
-- **世界模型定义差异**：志龙（强化学习方向）与赵昊老师（计算机视觉方向）就世界模型定义达成部分共识——CV界追求重建物理世界，可作为RL中世界模型的工具；分歧在于RL更强调可交互性，CV更强调三维表征，这一现状由学术发展阶段导致。**结论：世界模型在RL和CV界关注点不同，是否需要3D inductive bias由数据决定**。
-- **混合策略学习路线**：业界嘉宾、薛寒博士、王岳老师、李欣老师一致认为，当前阶段应采用混合方式，先模仿后强化是实际可行的路线。业界嘉宾分享公司采用模型强化加机理融合的方式，上层强化学习做决策、底层用MPC或DWA等传统方法执行；薛寒博士举例AlphaStar和GPT都是先模仿后强化，单独模仿或单独强化都不行；王岳老师认为PID有反馈，可作为强化学习的reward。**结论：复杂任务应先模仿后强化，当前阶段监督学习与强化学习各有局限，需融合使用**。
-- **仿真数据与真机数据结合**：主持人分享实验数据，300条仿真数据加20条真机数据可显著提升策略成功率，而纯仿真数据（300条）直接迁移真机成功率很低；薛寒博士认为reward数据是低成本方案，现实生活是最好的仿真器。**结论：仿真数据与真实数据结合是有效方案，仿真数据可覆盖物体随机位置与初始状态，少量真机数据用于微调**。
-- **数据质量把控**：杨立新老师与主持人就数据质量达成一致——视角固定与标定是影响模型表现的关键因素，Open X等数据集因相机视角不固定、缺少物体运动信息而质量受限；杨立新老师强调orkin从采集时记录物体运动，主持人提到自己洗ego4d数据集洗了三个月。**结论：数据采集需控制视角与标定，并记录物体运动信息**。
-- **无标注数据方向**：赵昊老师提出2025年应迈向大规模利用无标注真实数据，类比segment anything和depth anything的成功，认为不应再局限于讨论真实数据与仿真数据的比例（1:9、2:8、5:5等）。**结论：未来应重视无标注数据，作为有标注数据之外的第三个数据域**。
-- **国产仿真系统**：主持人提出中国是否强依赖英伟达生态的问题，赵昊老师回应称宋应团队在做国产替代生意，赌的是被卡脖子；赵昊老师认为技术上会统一，但business上复杂。**结论：国产仿真系统有市场需求，但产业问题复杂，技术标准化后问题不大**。
+**未形成统一结论**。本场讨论围绕具身形态、世界模型、策略学习路线与数据采集四个议题展开，各方观点存在明显分歧，但部分方向形成倾向性认识。
+**倾向性认识与主流意见**
+- **具身形态**：赵昊老师从第一性原理出发，认为**人形机器人与特种机器人将长期并存**——现实环境（桌椅等）为人形设计，人形机器人（含灵巧手）会占较大比例；特种机器人（机械臂等）已在工业生产中实现97%以上自动化，同样大量存在。王岳老师补充认为，大模型不应从上到下贯穿至硬件层，硬件变化时底层控制（小脑）应自适应，大脑层可保持不变。
+- **世界模型**：赵昊老师认为CV界追求重建物理世界，可作为RL中world models的调用工具，但当前三维视觉技术栈深、RL博士生难以完全掌握，导致RL领域不太关注三维表征；**是否需要3D归纳偏置由数据量决定**——数据少时需要更多归纳偏置，数据规模化后更端到端的方式可能更好。志龙从强化学习角度提出，world model第一要素是可交互（概念可追溯至1990-91年Sutton的Dyna-Q文章），其次才是物理规律与多模态信息。
+- **策略学习路线**：杨立新老师（业界）介绍公司实际采用**模型强化加机理融合**方式，因监督学习数据分布不足以覆盖高维动作空间、纯强化学习强依赖仿真环境且sim-to-real迁移困难。薛寒博士认为复杂任务应**先模仿后强化**，单独模仿或单独强化都不可行——模仿可提供先验信息降低样本复杂度，强化可超越专家水平。李欣老师认为两者并无本质冲突，核心是获取运动先验（latent），有数据用模仿学习、无数据用强化学习生成。
+- **数据采集**：薛寒博士主张**真实数据（reward采集）是当前更低成本方案**——现实生活本身就是最好的仿真器，柔性体任务（叠衣服、系鞋带等）现有仿真技术难以模拟；终极形态是脑机接口或可穿戴设备实现无感多模态采集。穆老师提出**仿真数据与真实数据互补**：300条仿真数据加上20条真机数据即可显著提升策略成功率，仿真数据可覆盖物体随机位置、姿态与初始状态。赵昊老师提出2025年应**推广大规模利用无标注真实数据**（如segment anything、depth anything范式），不再纠结真实与仿真数据的固定配比。
+**解决方案**
+- **硬件可靠性提升**：薛寒博士提出，具身智能训练与大规模真机评估需要高寿命、高可靠性的硬件，现有工业机械臂并非为此设计，需开发**个人柔顺硬件结构**以支撑规模化真机评估（依据：模型预测失误导致撞桌等事故，机器人易损坏，难以可靠scale up）。
+- **软硬件协同优化**：穆老师提出，具身智能应采用**软硬件协同进化范式**——以松龄产品两代迭代为例，第二代在遥操与策略部署上明显优于第一代；与任老师合作的凝胶夹爪可反馈触觉、摩擦力更优，硬件提升后算法同步受益。
+- **策略学习分层融合**：杨立新老师提出，当前阶段应采用**强化学习做上层决策、底层执行用传统方法（MPC、DWA等）**的分层方案，将强化学习的决策空间与任务设定严格限定，避免从观测直接学到电流控制的跨频率、跨规模难题（依据：公司实际部署经验）。
+- **真机reward获取**：王岳老师提出，凡PID能做的系统必然包含反馈，**可直接以该反馈作为强化学习执行过程中的reward**，解决真机复杂任务reward获取难题（依据：控制领域反馈是PID工作的必要条件）。
+- **数据质量管控**：杨立新老师提出，数据采集需**严格控制相机视角并做好标定**（手眼标定至今仍是未完全解决的问题），同时**记录物体运动信息**（刚体、关节体物理变化），而非仅采集本体关节角度与力矩（依据：Open X等数据集视角无法固定、缺少物体信息，影响策略表现）。
+- **仿真与真机数据配比**：穆老师提出，可用**海量仿真数据（覆盖随机位置、姿态、初始状态）配少量真机数据（约20条）**训练策略，成功率显著提升（依据：团队实验，300条仿真数据+20条真机数据，fenton方法微调）。
+- **国产仿真系统**：赵昊老师回应，已有团队（如宋应团队）布局国产替代以防卡脖子，但**产业问题复杂，技术最终会标准化统一，商业层面取决于脱钩与卡脖子风险判断**；具体是否强依赖英伟达生态，未提及。
 # 未决分歧与后续探索
-- **具身智能最终形态**：穆老师从机械领域提出，具身形态会收敛为人形机器人还是如《星际穿越》中可变形的大方块等特种形态，并指出机械领域有通过软手等硬件实现高顺应性抓取的「机械智能」路线；赵昊老师认为人形机器人和特种机器人将来都会存在，人形因现实环境为人设计而占很大比例，特种机器人已在车厂、微电子制造厂实现97%以上自动化。需验证的是人形与特种形态各自的应用边界与占比，暂无明确跟进方。
-- **大模型架构是否应完全端到端**：主持人提出是采用一个端到端模型，还是前段固定、后段接Action refiner的分层方案；王岳老师主张不应从上到下完全端到端，至少应分两层——大脑不变、小脑自适应肢体，并以人手断后大脑仍能工作、底层控制需适配新构型为例；赵昊老师认为若大模型直通最底层会消除硬件迭代可能性，新硬件出现时前段模型需完全重新训练。需验证分层架构在硬件更换时的重训成本与泛化能力，暂无明确跟进方。
-- **世界模型是否需要3D inductive bias**：赵昊老师认为CV界追求重建物理世界，UniSim等工作需要3D inductive bias，但数据规模扩大后可能不再需要，并梦想写一篇「data bias trade off」论文；志龙从强化学习角度认为世界模型第一要义是可交互，3D信息只是可引入的补充模态。赵昊老师提出由数据量决定，需验证数据规模与inductive bias需求之间的权衡关系，暂无明确跟进方。
-- **世界模型能否统一**：王岳老师以刺客信条游戏与真实世界跳楼结局不同为例，认为一个世界模型无法同时建模两个dynamics，世界模型可能做不到统一，但policy有可能统一；薛寒博士提出不同物理结构最后可有相同统一表征，王岳老师回应需加condition，工程难度高，M个独立模型比一个高维可控模型更简单。需验证统一世界模型在工程上的可实现性与复杂度，暂无明确跟进方。
-- **强化学习与模仿学习的最终路线**：业界嘉宾认为当前阶段监督学习数据量不足、仿真环境不够好，应采用模型强化加机理融合的混合方式；薛寒博士认为复杂任务应先模仿后强化，单独模仿或单独强化都不行，并以AlphaStar和GPT为例；李欣老师认为两者并不冲突，只是获取运动先验的不同方式。需验证先模仿后强化在工程上能否解决学术界宣称的「先模仿再强化会不好」的问题，暂无明确跟进方。
-- **真机reward获取方式**：主持人提出若以RL作为最后环节，真机复杂任务的reward如何获取，因仿真有上帝视角而真机传感器有偏差；王岳老师认为PID能做的系统必然有反馈，可完全拿该反馈作为强化学习的reward。需验证该反馈作为reward在复杂任务中的有效性，暂无明确跟进方。
-- **中国是否强依赖英伟达生态**：主持人提出Isaac Sim/Isaac Lab是目前最好用的柔性物体仿真接口，询问未来中国是否强依赖英伟达生态，还是能有国产产品支持仿真；赵昊老师回应朋友宋应赌国产替代、认为会被卡脖子，技术上会统一但business上复杂。需验证国产仿真系统的可行性与产业路径，暂无明确跟进方。
-- **数据采集路线**：薛寒博士主张all in reward采集，认为现实生活是最好的仿真器，终极形态是脑机接口或机电等可穿戴设备实现无感多模态采集；主持人认为仿真数据可提供海量随机初始状态，配合少量真机数据（如300条仿真加20条真机）可显著提升成功率；赵昊老师认为真实数据还是仿真数据要看成本，case by case，并主张2025年应推广无标注真实数据的大规模利用。需验证可穿戴设备采集的精度能否覆盖遥操数据的gap，以及无标注数据在具身智能中的有效性，暂无明确跟进方。</t>
+- **具身智能最终形态**：穆老师提出具身智能最终会收敛成人形机器人还是科幻片中可变形的大方块（如《星际穿越》），并引出机械领域「机械智能」概念——软手靠摩擦与顺应性可在较大误差下抓牢物体。赵昊老师从第一性原理出发，认为现实中桌椅等设施为人设计，人形机器人（双足或轮式、带灵巧手）会占很大比例，同时特种机器人（如车厂、微电子制造厂已实现97%以上自动化的机械臂）也会大量存在。分歧点在于人形与特种形态的占比与收敛方向，需验证的是不同形态在成本与任务适配上的长期表现。
+- **大模型是否应自上而下贯穿**：王岳老师主张大模型不应从最上层直通最底层，否则新硬件（尤其软体机器人）出现时需完全重新训练；他以人手受伤后大脑仍能工作、小脑需自适应新肢体为例，认为至少应分大脑与小脑两层，底层控制需adaptive到肢体。穆老师则持软硬件协同优化观点，以松龄两代产品、凝胶夹爪（可反馈触觉、更稳、摩擦力更好）为例说明协同进化。分歧点在于模型分层与端到端程度，需验证的是分层架构在硬件迭代时的迁移成本与性能。
+- **世界模型是否需要3D归纳偏置**：赵昊老师认为CV界追求重建物理世界（3D、空间、物理规律），可作为RL中world models的工具，但当前三维视觉技术栈深、RL博士生难以完全学习；他提出「data bias trade off」设想——数据多时所需归纳偏置少、数据少时所需多，并以ImageNet、GPT的成功说明大规模学习可减少归纳偏置，而UniSim等近期工作又需要3D归纳偏置。志龙从强化学习角度提出世界模型第一要素是可交互（可追溯至1990-91年Sutton的Dyna-Q），其次才是物理规律与3D信息。分歧点在于世界模型是否必须引入3D归纳偏置，需验证的是数据规模增长后归纳偏置需求是否下降。
+- **世界模型能否统一**：王岳老师以游戏主角跳楼在游戏与物理世界结局不同为例，认为一个世界模型无法同时建模两个dynamics（相同输入、不同输出），世界模型可能做不到统一，但policy有可能统一——人作为同一玩家可在游戏中跳楼、在现实中避免跳楼。薛寒博士提出反对意见，认为可在世界模型中加condition（如「这是游戏还是真实」）实现统一，但王岳老师回应称M个独立模型比一个高维可控condition模型更简单，且目前没有atari game能靠一个世界模型建模所有游戏。分歧点在于统一世界模型与多个独立模型的可实现性，需验证的是高维condition模型的训练复杂度与泛化能力。
+- **强化学习与模仿学习的最终路线**：杨立新老师（业界）介绍公司采用模型强化加机理融合方式，认为监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境、sim-to-real迁移困难，现阶段应限制强化学习的决策空间与任务设定。薛寒博士认为复杂任务应先模仿后强化，单独模仿无法达到专家水平（除非任务就是模仿专家），单独强化样本复杂度不可接受；他反驳「先模仿再强化会不好」的学术论文结论，认为工程手段可解决。李欣老师认为两者并无本质冲突，只是想要运动先验——有数据可用模仿学习，无数据可用强化学习生成。分歧点在于最终收敛到单一方法还是混合方案，需验证的是先模仿后强化在具身任务中的实际效果与样本效率。
+- **真机reward如何获取**：穆老师提出若以强化学习作为最后环节，真机复杂任务的reward获取存在困难——仿真中有上帝视角，真机上detection与传感器有偏差。王岳老师回应称PID能做的系统必然有反馈，可完全拿该反馈作为强化学习的reward，过去用PID效果不够好，现在通过强化可做得更好。分歧点在于真机reward的可靠来源，需验证的是基于PID反馈的reward设计在复杂任务中的适用性。
+- **仿真数据与真实数据的比例**：穆老师介绍实验显示300条仿真数据加上20条真机数据即可显著提升成功率，认为仿真数据可覆盖物体随机位置、orientation与初始状态，真机数据补充精度。赵昊老师认为应case by case看成本——室内服务机器人真机数据可行，自动驾驶corner case危险且麻烦；他提出2025年应加入第三个domain「无标注真实数据」，像segment anything、depth anything那样大规模利用，不再纠结1:9、2:8、5:5的比例问题。分歧点在于仿真与真实数据的最优配比及无标注数据的价值，需验证的是无标注数据在具身任务中的实际增益。
+- **国产仿真系统能否替代英伟达生态**：穆老师提出中国是否强依赖英伟达生态（Isaac Sim/Isaac Lab目前支持柔性物体仿真接口），还是能有国产产品支持仿真。赵昊老师回应称宋应等团队赌的是「会被卡脖子」、在做国产替代，这是business层面的复杂问题，技术上最终会比较统一，但暂时不会直接触碰该生意。分歧点在于国产仿真系统的可行性与商业路径，需验证的是国产替代在技术成熟度与生态建设上的进展。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>74.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/5085</t>
+          <t>21458/6169</t>
         </is>
       </c>
     </row>
@@ -2929,72 +2939,41 @@
       <c r="C7" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司（东源煤电）、云南东源曲靖电力有限公司（曲靖电力）、招银金融租赁有限公司（招银租赁）金融借款合同纠纷上诉案，由最高人民法院二审公开开庭审理。合议庭由审判长李少平及审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。各方当事人对出庭人员身份均无异议，东源煤电、东源煤业、曲靖电力合并发表意见。庭审围绕三个争议焦点展开：国开行抵押权是否构成善意取得、一审判决对罚息复利计算及起算日期是否认定错误、东源煤电及东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方均无异议，合议庭予以确认，庭后出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司（东源煤电）、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷上诉案，不服云南省高级人民法院（2018）云民初88号民事判决，向最高人民法院提起上诉。二审公开开庭审理，合议庭由审判长李少平与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。各方围绕三个争议焦点展开辩论：国开行抵押权是否构成善意取得、罚息复利计算及起算日期、东源煤电及东源煤业是否应连带给付违约金。经合议庭评议提出调解方案，各方均无异议，合议庭予以确认，庭后出具调解书。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国家开发银行） | 请求撤销一审判决相关判项，改判支持其利息、罚息、复利计算主张及违约金请求 | 东源煤电利息支付截止2017年12月20日，利息应自2017年12月21日计算至2018年6月12日，合计21,795,727.68元；2018年6月13日发函要求偿还，罚息自2018年6月13日计算至2019年2月19日，合计41,050,579.57元；复利自2018年3月21日计算至2019年2月19日，合计1,918,206.23元。依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金，且未配合办理账户管理及柜台前移手续。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 国开行宣布贷款提前到期未给合理期限，违反合同第24条第2款第2项限期偿还约定；罚息不应作为复利基数，依据人民币利率管理规定第21条及合同第6条第4款，均未提及罚息计收复利；国开行未举证证明东源煤电违反柜台前移和账户管理，且未按合同约定发出限期纠正函，无权主张违约金。 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 国开行未在抵押时点（2015年12月）查询融资租赁登记系统，不构成善意取得；东源煤电出资行为系无权处分，因招银租赁2012年已取得设备所有权；国开行审查义务应扩展至东源煤电，因其系借款人兼抵押人全资控股母公司。 |
-| 上诉人（国家开发银行） | 请求确认抵押权有效，构成善意取得 | 已按央行规定查询融资租赁登记系统，曲靖电力公司名下无登记记录，且至今仍无记录；抵押设备为通用设备无唯一标识码，无法通过设备查询；审查义务仅限于抵押人曲靖电力公司，不能扩大到关联企业；已对设备所有权尽审慎义务，权属证明显示所有权属曲靖电力。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 2015年12月2日邮件已用红色标注设备名称一致，国开行应尽注意义务；国开行未提供证据证明已做区分，应承担不利后果。 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 国开行应提供2015年12月抵押时点的查询结果，而非2018年9月的查询证书；融资租赁登记具有对抗效力，国开行未查询即不构成善意；案涉5套设备无唯一识别码，登记时未填写，但租赁物清单已作为附件上传，载明存放地点为恩洪矿区煤矸石电厂。 |
-| 上诉人（国家开发银行） | 请求支持其利息、罚息、复利计算主张 | 合同第6条第4款明确约定对逾期借款利息按罚息利率计收复利，不违反法律强制性规定；东源煤电未上诉，一审已支持罚息复利，应维持。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 合同第6条第4款表述为利息计收复利，未提及罚息，约定不明确；最高人民法院2015年、2016年判例支持罚息不能作为复利基数；合同系国开行提供格式文本，应作不利于提供方解释。 |
-| 上诉人（国家开发银行） | 请求支持违约金请求 | 借款合同第24条第3项明确约定违约金为千分之一；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续，举证责任在被上诉人。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 国开行未举证证明东源煤电违反柜台前移和账户管理；国开行未按合同约定发出限期纠正函，无权主张违约金。 |
-| 被上诉人（招银租赁） | 尊重合议庭审查结果 | 招银租赁非国开行与东源煤电借款合同当事人，不参与相关争议。 |
-| 上诉人（国家开发银行） | 请求确认抵押权有效，构成善意取得 | 已按央行规定查询融资租赁登记系统，曲靖电力公司名下无登记记录，且至今仍无记录；抵押设备为通用设备无唯一标识码，无法通过设备查询；审查义务仅限于抵押人曲靖电力公司，不能扩大到关联企业；已对设备所有权尽审慎义务，权属证明显示所有权属曲靖电力。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 2015年12月2日邮件已用红色标注设备名称一致，国开行应尽注意义务；国开行未提供证据证明已做区分，应承担不利后果。 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 国开行应提供2015年12月抵押时点的查询结果，而非2018年9月的查询证书；融资租赁登记具有对抗效力，国开行未查询即不构成善意；案涉5套设备无唯一识别码，登记时未填写，但租赁物清单已作为附件上传，载明存放地点为恩洪矿区煤矸石电厂。 |
-| 上诉人（国家开发银行） | 请求支持其利息、罚息、复利计算主张 | 合同第6条第4款明确约定对逾期借款利息按罚息利率计收复利，不违反法律强制性规定；东源煤电未上诉，一审已支持罚息复利，应维持。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 合同第6条第4款表述为利息计收复利，未提及罚息，约定不明确；最高人民法院2015年、2016年判例支持罚息不能作为复利基数；合同系国开行提供格式文本，应作不利于提供方解释。 |
-| 上诉人（国家开发银行） | 请求支持违约金请求 | 借款合同第24条第3项明确约定违约金为千分之一；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续，举证责任在被上诉人。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 国开行未举证证明东源煤电违反柜台前移和账户管理；国开行未按合同约定发出限期纠正函，无权主张违约金。 |
-| 被上诉人（招银租赁） | 尊重合议庭审查结果 | 招银租赁非国开行与东源煤电借款合同当事人，不参与相关争议。 |
+| 上诉人（国开行） | 请求撤销一审判决，改判支持其抵押权、罚息复利计算及违约金主张 | 主张抵押设备为通用设备、无唯一标识码，审查义务仅限于抵押人曲靖电力公司，查询融资租赁系统无记录，构成善意取得；主张利息自2017年12月21日计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；主张依据借款合同第24条第3项，东源煤电未配合办理账户管理及柜台前移手续，应支付千分之一违约金 |
 # 举证与法庭调查
 **证据与质证意见**
-- **东源方邮件证据**：东源方主张2015年12月2日邮件中融资情况统计表载明招银租赁抵押物为恩洪电厂设备资产、抵押手续已登记，国开行抵押物为恩洪电厂设备在建工程、正在办理，且设备名称完全一致、用红色标注，国开行应尽注意义务；国开行反驳称邮件系贷后审查材料，统计表并列描述不能得出已告知的结论，且2015年12月2日邮件与12月22日签订抵押合同时间吻合，贷后审查报表应在次年年初提供。
-- **国开行融资租赁查询证书**：国开行提交2018年9月对曲靖电力公司的融资租赁查询证书，主张已尽查询义务；招银租赁质证称该证书不符合要求，依据2014年93号中国人民银行规定，国开行应提供2015年12月抵押时点的查询结果。
-- **招银租赁回租设备清单**：招银租赁一审提交回租设备清单（证据第7页），仅载明设备名称和生产厂家，未载明型号，出厂日期为2012年3月1日；国开行质证称现场调查核实抵押设备铭牌生产日期均在2013年以后（部分2013年11月、12月，部分2014年3月），看不出是同一设备。
-- **权属证明材料**：国开行提交证据第54页、58页，显示东源煤电、曲靖电力对设备权属的证明材料和股东会决议，证明设备所有权属曲靖电力；国开行据此主张已尽审慎义务，融资租赁登记核查义务仅限于曲靖电力公司。
-- **融资租赁登记核查表**：国开行提交证据第108页核查表，显示曲靖电力公司名下无融资租赁登记信息，主张已按法律法规和行业规范履行义务，构成善意取得。
-- **审计报告**：招银租赁一审提交2013年和2015年审计报告（证据第82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行据此主张招银租赁知道或应当知道设备出资情况。
+- **东源方2015年12月2日邮件及融资情况统计表**：东源方主张该邮件显示招银租赁抵押物已登记、国开行抵押物正在办理，设备名称完全相同且用红色标注，国开行应尽注意义务；国开行反驳称邮件正文及附表均无告知融资租赁的文字，统计表仅并列描述，不能得出已告知的结论。
+- **国开行2018年9月融资租赁查询证书**：国开行用以证明查询无记录；招银租赁质证认为该查询不符合要求，依据2014年93号文，国开行应在抵押时点（2015年12月）查询人行征信中心。
+- **招银租赁回租设备清单（证据第7页）**：招银租赁用以证明设备特定化；国开行质证称清单仅载明设备名称和生产厂家，无型号，且出厂日期为2012年3月1日，与国开行现场调查的铭牌生产日期（2013年11月、12月、2014年3月）不符，不能认定为同一设备。
+- **国开行证据第54、58页权属证明及股东会决议**：国开行用以证明抵押设备所有权属曲靖电力公司；招银租赁未否认，但主张东源煤电出资系无权处分。
+- **国开行证据第108页融资租赁登记核查表**：国开行用以证明已对曲靖电力公司进行核查；招银租赁主张应扩大至东源煤电。
+- **招银租赁2013年、2015年审计报告（证据第82、95页）**：招银租赁用以证明曲靖电力公司注册资本4亿元已实缴；国开行用以证明设备出资事项已载明。
 **法官询问要点**
-- **融资租赁登记性质**：审判长询问各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果；国开行认为系行业强制性规范，目的是防范金融风险；招银租赁认为系权利公示，具有对抗效力，但不影响所有权设立转移；东源方认为系行业指导性规范，不当然产生物权后果。
-- **查询方式**：审判员王海峰询问融资租赁登记系统有几种查询方式；国开行称仅能按查询单位查询；招银租赁称可按公司名称或设备查询，但设备查询涉及种类物区分问题。
-- **设备识别码登记**：审判员询问案涉5套设备识别码是否登记清楚；招银租赁称设备系种类物，无唯一识别码，当时未登记；审判员追问设备安装后发电机上是否有唯一标识码，招银租赁称铭牌上只有型号和参数，上海电气出厂的同型号设备铭牌相同。
-- **内部风控规定**：审判员询问国开行贷款前审查是否有内部规定要求必须查询融资租赁系统并保留未查询到结果的单子；国开行称按央行规定查询，因无记录未保留筛查记录，内部无此规定。
-- **查询义务程度**：审判员询问违反查询规范多大程度导致融资租赁司法解释第9条第2款后果，是基本查询义务还是全面审慎义务；国开行主张基本义务，招银租赁主张严格义务，未查询即不构成善意。
-- **其他途径知晓**：审判员询问若银行通过其他途径知晓抵押物属融资租赁物，是否相当于已了解风控情况；国开行称基本义务必须履行，招银租赁称仍须通过央行系统查询，因其他途径无法证明。
-- **举证责任分担**：审判员询问融资租赁司法解释第9条第2款举证责任如何分担；国开行主张按谁主张谁举证原则，招银租赁主张第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
-- **登记信息冲突**：审判长询问各方如何看待不同登记机构产生的登记信息冲突及建议；国开行认为系系统信息不完整、条块化分割问题，招银租赁建议从立法、行业协会、技术层面改进。
+- **融资租赁登记性质及法律后果**：审判长询问各方对中国人民银行征信中心融资租赁登记性质及法律后果的理解。国开行认为是行业强制性规范，旨在防范金融风险；东源方认为是行业指导性规范，不当然产生物权后果；招银租赁认为是权利公示，产生对抗效力，不影响所有权设立转移。
+- **查询方式**：王海峰法官询问融资租赁登记系统有几种查询方式。国开行称仅能按查询单位查询；招银租赁称可按公司名称或设备查询，但设备查询涉及种类物区分问题。
+- **案涉设备识别码登记情况**：王海峰法官询问案涉5套设备识别码是否登记清楚。招银租赁称设备为种类物，无唯一识别码，未登记。
+- **内部风控规定**：葛洪涛法官询问国开行贷款前审查是否有内部规定要求保留未查询到结果的单证。国开行称无此规定，因未查询到结果故未保留。
+- **查询义务程度**：葛洪涛法官询问违反查询规范达到何种程度才导致融资租赁司法解释第9条第2款后果，是基本查询义务还是全面审慎义务。国开行认为是基本义务，招银租赁认为是严格义务，未查询即不构成善意。
+- **举证责任分担**：葛洪涛法官询问各方对融资租赁司法解释第9条第2款举证责任分担的理解。国开行主张谁主张谁举证；招银租赁主张第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
 **双方辩论的争议焦点**
-- **告知义务是否履行**：东源方主张2015年12月2日邮件已告知设备抵押情况，国开行应尽注意义务；国开行主张邮件系贷后审查材料，统计表并列描述不能得出已告知结论，且招银租赁栏记载的抵押类型为不动产抵押，与融资租赁是两个法律概念。
-- **审查义务范围**：国开行主张其审查义务仅限于抵押人曲靖电力公司，不能扩大到关联企业；招银租赁主张东源煤电系借款人兼抵押人全资控股母公司，国开行应调查东源煤电的权属完整性。
-- **设备所有权归属**：招银租赁主张2012年设备交付时即取得所有权，东源煤电出资行为系无权处分；国开行主张设备系通用设备无唯一标识码，已对抵押人系统查询无记录，且权属证明显示所有权属曲靖电力。
-- **是否构成善意取得**：国开行主张已尽审慎义务，构成善意取得；招银租赁主张国开行未在抵押时点查询，不构成善意。
-- **上海中院判决影响**：国开行主张上海中院判决仅限返还义务，未确认所有权归属，与本案抵押权审理不冲突；招银租赁未直接回应。
+- **国开行抵押权是否构成善意取得**：国开行主张抵押设备为通用设备、无唯一标识码，审查义务仅限于抵押人曲靖电力公司，查询无记录即构成善意；东源方主张邮件已告知融资租赁情况，国开行未尽注意义务；招银租赁主张国开行未在抵押时点查询，不构成善意。
+- **融资租赁登记查询义务范围**：国开行主张仅限于抵押人曲靖电力公司；招银租赁主张因东源煤电系借款人及全资控股母公司，应扩大至东源煤电。
+- **东源煤电出资行为性质**：招银租赁主张系无权处分，因2012年已取得设备所有权；国开行主张设备已实缴出资，所有权属曲靖电力公司。
+- **上海中院判决与本案关系**：国开行主张上海中院判决仅确认返还义务，未确认所有权归属，与本案担保物权审理不冲突；招银租赁未明确回应。
 # 庭审结果
-**争议焦点归纳**
-- **争议焦点一**：国开行抵押权是否构成善意取得。国开行主张已尽审查义务，抵押设备为通用设备无唯一标识码，且已查询融资租赁登记系统无记录，构成善意取得；东源方主张国开行未尽注意义务，因邮件中已用红色标注设备名称一致；招银租赁主张国开行未在抵押时点查询，不构成善意。
-- **争议焦点二**：一审判决对案涉借款罚息复利计算及起算日期是否认定错误。国开行主张利息自2017年12月21日计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；东源方主张国开行宣布贷款提前到期未给合理期限，且罚息不应作为复利基数。
-- **争议焦点三**：东源煤电、东源煤业是否应连带给付违约金。国开行主张依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金，且未配合办理账户管理及柜台前移手续；东源方主张国开行未举证证明违约行为，且未按合同约定发出限期纠正函。
-**庭审结果**
-- **调解方案**：合议庭休庭评议后提出调解方案，各方当事人均无异议，合议庭予以确认，庭后出具调解书。
-- **债权确认**：国开行对东源煤电债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元；招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权，招银租赁对6项设备有所有权。
-- **设备处置**：招银租赁和国开行对案涉全部发电设备整体盘活处置，变现价款双方各得50%，费用各担50%；调解书生效后20日内，国开行向一审法院提出执行申请，启动司法处置程序。
-- **后续安排**：若破产管理人不将招银租赁债权纳入预留方案，由东源煤电按有担保清偿方案清偿；若司法变现不能，国开行和招银租赁放弃案涉设备权益，由东源曲靖电力自主生产经营；案涉设备管理费用由东源曲靖电力承担，东源曲靖电力无条件配合司法处置。
-- **费用承担**：一审判决第2项、第4项无争议，按判项内容确认；一审诉讼费用中招银租赁诉请部分由二审法院计算后由国开行承担，二审诉讼费用由国开行和东源煤电各承担50%。
-- **未决事项**：协议签订后各方就本案问题不再存在任何争议。</t>
+本案争议焦点归纳为三项：一是国开行抵押权是否构成善意取得；二是一审判决对案涉借款罚息、复息计算及起算日期是否认定错误；三是东源煤电、东源煤业是否应连带给付违约金。经合议庭休庭评议，提出调解方案，各方均无异议，合议庭予以确认，庭后出具调解书。调解方案主要内容：国开行对东源煤电债权扣除破产已清偿本金外，利息、罚息、复利合计6474.4513万元；招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权，招银租赁对6项设备有所有权；招银租赁和国开行对案涉全部发电设备整体盘活处置，变现价款双方各得50%，实现费用各担50%；调解书生效后20日内由国开行向一审法院提出执行申请，启动司法处置程序；未实现债权待执行法院出具体本裁定后按破产重整计划预留方案实现，若破产管理人不纳入预留方案，由东源煤电按有担保清偿方案清偿；若司法变现不能，国开行和招银租赁放弃案涉设备权益，由东源曲靖电力自主生产经营；案涉设备管理费用由东源曲靖电力承担，东源曲靖电力无条件配合司法处置；一审判决第2项、第4项无争议按判项内容确认；一审诉讼费中国开行诉请部分按一审判决执行，招银租赁诉请部分由二审法院按规定计算后由国开行承担；二审诉讼费由国开行和东源煤电各承担50%；协议签订后各方就本案涉及问题不再存在任何争议。审判长指出，本案涉及的动产抵押权与融资租赁物所有权冲突是司法实践中的普遍性难题，根本原因在于国家尚未建立统一的动产登记制度，现有动产融资租赁登记系统和动产抵押登记系统缺乏有效衔接，合议庭将根据最高人民法院关于加强司法建议工作的意见向有关部门提出司法建议。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>113.5</v>
+        <v>96</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/5651</t>
+          <t>28485/2741</t>
         </is>
       </c>
     </row>
@@ -3151,49 +3130,49 @@
       <c r="C8" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持并汇报，合作局领导金昌柱、公司国内领导林总及管理组、技术组相关人员参会。验收组于18号、19号提前介入项目摸排，20号召开首次会议，目前已完成卢萨卡点（除带料加工调试外）和蒙蒙泽点的全部验收工作，姆皮卡点内业资料已提前拿到卢萨卡点。验收工作分内业检查和外业检查，专业方向涵盖建筑工程、安装工程和机电设备。
-内业方面，项目执行团队基本能保证主要人员在岗，编制了施工组织计划、管理计划、实施细则和专项预案，内业资料基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但资料分散，需汇总到卢萨卡分类成册，且存在分类整理和签字规范性需完善的问题。外业方面，建筑部分主要建材从国内采购或从卢萨卡集中预制采购，内在品质和外观达到较好标准；安装部分钢结构材料从国内定制发货，施工工艺和外观质量满足规范要求；设备部分参照中国标准定制，由中粮西安设计院及厂家供货，蒙蒙泽点设备投料试运行正常，产能经打表计算符合设计指标。财务方面，账户设置、资金往来、银行开户等过程完全符合财务处理规范和标准，中基公司在此项目是第一个也是唯一一个项目，没有挪用资金的情况。
-验收组提出整改要求：人员履约方面，个别人员进出场时间、护照及证件有效期需完善，人员统计需包含厂家服务人员；内业资料需按规范分类整理，签字规范性需完善，资料需汇总到卢萨卡分类成册；现场实体方面，局部装饰装修损伤需检查修补，厂区排水需清理排查，混凝土路面开裂需处理，监控管线接头脱落需检查，提升通道需考虑防雨水倒灌，廊桥竖条需加密。管理组田组长表示会后与技术组细化问题并制定方案处理，技术组龚总汇报人员统计和护照收集已开展，内业资料将严格按要求汇总，现场实体将编制方案逐一整改。合作局领导金昌柱要求相关方尽快补充资料，与验收组做好沟通，避免遗留未决事项；
-要求管理组和总包单位共同分析蒙蒙泽厂区混凝土路面开裂原因，制定科学合理的整改方案，最迟在出报告前完成整改，验收组需复核；要求做好成品保护，及时修补破损。公司领导林总要求按照商务部经商局指示完成验收任务，按合同规章制度仔细验收，并提醒注意交通安全，姆皮卡路况不好，且赞比亚雨季已到。验收组补充说明不可预见费使用情况，本项目有动用不可预见费的情况，有关依据证据和数据必须做到充分无误，后续将专门对接完善资料。
+本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持并汇报。验收组于18号、19号提前介入项目摸排，20号召开首次会议，目前已完成卢萨卡点（除带料加工调试外）和蒙蒙泽点的全部验收工作，蒙蒙泽点顺带完成带料调试和试生产，工艺设备运行正常，产能符合设计指标。姆皮卡点内业资料已提前拿到卢萨卡点，现场验收尚未开展。内业检查方面，项目执行团队基本能保证主要人员在岗，编制了施工组织计划、管理计划、实施细则和专项预案，内业资料基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但资料分散，需汇总到卢萨卡分类成册，签字规范性需完善。外业检查方面，建筑、安装、设备三个板块总体评价良好，主要建材从国内采购或从卢萨卡集中预制采购，钢结构材料从国内定制发货，设备参照中国标准定制，由中粮西安设计院及厂家供货，现场安装调试正常，机电设备安装符合国家质量检验标准。
+财务检查方面，财务从账户设置、资金往来、银行开户等过程完全符合财务处理规范和标准，中基公司在此处是第一个项目，也是唯一项目，没有挪用资金的情况。验收组提出整改项要求：人员履约方面，个别人员进出场时间、护照及证件有效期需完善，人员统计需包含厂家服务人员；内业资料方面，分类整理和签字规范性需完善，资料需汇总到卢萨卡分类成册；现场实体方面，局部装饰装修损伤需检查修补，厂区排水需清理排查，混凝土路面开裂需处理，监控管线接头脱落需检查，提升通道需防雨水倒灌，廊桥竖条需加密。管理组田组长表示会后与技术组细化问题并制定方案处理，技术组龚总汇报人员统计和护照收集已开展，内业资料将严格按要求汇总，现场实体将编制方案逐一整改。合作局领导金昌柱强调：相关方尽快补充资料，与验收组沟通对接，不留遗留未决事项；重视蒙蒙泽厂区混凝土路面开裂问题，分析原因并制定切实可行的整改方案；研究出技术方案后尽快整改，最迟在出报告前完成整改，验收组需复核；做好成品保护，及时修补破损。
+公司国内领导林总要求按合同规章制度标准仔细验收，提醒当地用户建议，注意交通安全和疫情防控。验收组补充说明不可预见费使用情况：本项目有动用不可预见费的情况，原则上在原合同、原设计、原投资控制基础上增加动用，有关依据证据和数据必须做到充分无误，验收组将继续跟踪和完善相关资料。
 # 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 内业检查 | 项目执行团队基本能保证主要人员在岗，编制了施工组织计划、管理计划、实施细则和专项预案，内业资料基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但资料分散，需汇总到卢萨卡分类成册，且存在分类整理和签字规范性需完善的问题。 | 🔄进行中 |
-| 外业检查-建筑 | 主要建材从国内采购或从卢萨卡集中预制采购，内在品质和外观达到较好标准，但存在局部装饰装修损伤、厂区排水需清理排查、混凝土路面开裂等问题。 | 🔄进行中 |
-| 外业检查-安装 | 钢结构材料从国内定制发货，施工工艺和外观质量满足规范要求，但监控管线接头脱落需检查，提升通道需考虑防雨水倒灌，廊桥竖条需加密。 | 🔄进行中 |
-| 外业检查-设备 | 设备参照中国标准定制，由中粮西安设计院及厂家供货，蒙蒙泽点设备投料试运行正常，产能经打表计算符合设计指标。 | ✅已完成 |
-| 财务检查 | 账户设置、资金往来、银行开户等过程完全符合财务处理规范和标准，中基公司在此项目是第一个也是唯一一个项目，没有挪用资金的情况。 | ✅已完成 |
-| 人员履约 | 个别人员进出场时间、护照及证件有效期需完善，人员统计需包含厂家服务人员。 | 🔄进行中 |
-| 内业资料 | 需按规范分类整理，签字规范性需完善，资料需汇总到卢萨卡分类成册。 | 🔄进行中 |
-| 现场实体 | 局部装饰装修损伤需检查修补，厂区排水需清理排查，混凝土路面开裂需处理，监控管线接头脱落需检查，提升通道需考虑防雨水倒灌，廊桥竖条需加密。 | 🔄进行中 |
+| 验收工作总体 | 验收组于18号、19号提前介入项目摸排，20号召开首次会议；卢萨卡点已完成除带料加工调试以外的所有验收工作，蒙蒙泽点已完成全部验收工作，姆皮卡点内业资料已提前拿到卢萨卡点，现场验收尚未开展。 | 🔄进行中 |
+| 内业检查 | 项目执行团队基本能保证主要人员在岗，编制了施工组织计划、管理计划、实施细则和专项预案；内业资料基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但资料分散，需汇总到卢萨卡分类成册，签字规范性需完善。 | 🔄进行中 |
+| 外业检查-建筑 | 主要建材从国内采购或从卢萨卡集中预制采购，内在品质和外观达到较好标准；局部装饰装修损伤需检查修补，厂区排水需清理排查，混凝土路面开裂需处理。 | 🔄进行中 |
+| 外业检查-安装 | 钢结构材料从国内定制发货，施工工艺和外观质量满足规范要求；监控管线接头脱落需检查，提升通道需防雨水倒灌，廊桥竖条需加密。 | 🔄进行中 |
+| 外业检查-设备 | 设备参照中国标准定制，由中粮西安设计院及厂家供货，现场安装调试正常；蒙蒙泽点工艺设备运行正常，产能符合设计指标，机电设备安装符合国家质量检验标准。 | ✅已完成 |
+| 财务检查 | 财务从账户设置、资金往来、银行开户等过程完全符合财务处理规范和标准；中基公司在此处是第一个项目，也是唯一项目，没有挪用资金的情况。 | ✅已完成 |
+| 整改项-人员履约 | 个别人员进出场时间、护照及证件有效期需完善，人员统计需包含厂家服务人员；技术组已开展人员统计和护照收集工作。 | 🔄进行中 |
+| 整改项-内业资料 | 分类整理和签字规范性需完善，资料需汇总到卢萨卡分类成册；技术组承诺在验收完成第一时间将三个厂区资料全部汇总于卢萨卡，包括竣工图分类汇总、分类组卷及编码。 | 🔄进行中 |
+| 整改项-现场实体 | 局部装饰装修损伤需检查修补，厂区排水需清理排查，混凝土路面开裂需处理，监控管线接头脱落需检查，提升通道需防雨水倒灌，廊桥竖条需加密；技术组承诺编制现场实体整改方案并逐一整改落实。 | 🔄进行中 |
+| 不可预见费使用 | 本项目有动用不可预见费的情况，原则上在原合同、原设计、原投资控制基础上增加动用，有关依据证据和数据必须做到充分无误；验收组将继续跟踪和完善相关资料。 | 🔄进行中 |
 # 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 蒙蒙泽厂区混凝土路面开裂 | 中 | 可能影响项目移交后的外观和耐久性，存在大面积开裂隐患 | 管理组、总包单位 | 共同分析原因，制定科学合理的整改方案，最迟在出报告前完成整改，验收组复核 |
+| 蒙蒙泽厂区混凝土路面开裂 | 高 | 可能影响项目移交后使用，存在大面积开裂隐患 | 管理组、总包单位、验收组王总 | 分析成因（气候、施工工艺、材料），制定切实可行整改方案，最迟在出报告前完成整改，验收组复核 |
 | 监控管线接头脱落 | 中 | 可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
-| 提升通道雨水倒灌 | 中 | 雨水倒灌可能影响设备运行 | 施工组 | 考虑技术措施解决，如增加覆盖面积 |
-| 廊桥竖条分布不足 | 低 | 存在安全隐患，影响巡检和维护人员安全 | 施工组 | 中间再加两个竖条，增加安全保障 |
-| 局部装饰装修损伤 | 低 | 影响交付外观 | 施工组 | 检查修补，打扫卫生 |
-| 厂区排水系统阻塞 | 中 | 雨季来临可能导致积水 | 施工组 | 最后清理和排查，确保排水畅通 |
-| 资料分散 | 中 | 存在汇总不及时的风险 | 执行单位 | 会后将三个厂区的资料全部汇总至卢萨卡，分类组卷及编码 |
-| 个别特种人员证件有效期过期 | 中 | 存在合规风险 | 执行单位 | 与国内人力资源对接，完善证件延期或更新 |
-| 姆皮卡点路途遥远、路况不好 | 中 | 存在交通安全风险 | 验收组 | 注意交通安全，做好疫情防控 |
-| 赞比亚雨季已到 | 中 | 可能影响验收工作 | 验收组 | 注意交通安全，做好疫情防控 |
+| 卢萨卡点提升通道雨水倒灌 | 中 | 雨水可能倒灌，影响设备运行 | 施工组 | 检查原设计，考虑增加覆盖面积或技术措施 |
+| 廊桥竖条分布较少 | 低 | 存在安全隐患，影响巡检维护人员安全 | 施工组 | 中间再加两个竖条，增强视觉安全感 |
+| 姆皮卡点路途遥远、路况差 | 高 | 存在交通安全风险 | 验收组 | 注意交通安全，做好疫情防控 |
+| 赞比亚雨季来临 | 中 | 厂区排水可能阻塞，影响成品保护 | 施工组 | 检查厂区排水，清理屋面及室外通道，做好成品保护 |
+| 人员履约资料不完善 | 中 | 影响验收报告闭合 | 管理组、技术组 | 完善人员进出场时间、护照及证件有效期，统计厂家服务人员 |
+| 内业资料分散、签字不规范 | 中 | 影响竣工文件组卷成册 | 技术组 | 汇总至卢萨卡分类成册，规范签字 |
+| 不可预见费使用资料不完善 | 中 | 影响验收报告准确性 | 验收组、施工单位 | 完善依据证据和数据，确保充分无误 |
 # 后续计划
-- **资料汇总**：执行单位会后将三个厂区的资料全部汇总至卢萨卡，包括竣工图，进行分类汇总、分类组卷及编码。
-- **路面开裂整改**：管理组和总包单位共同分析蒙蒙泽厂区混凝土路面开裂原因，制定科学合理的整改方案，最迟在出报告前完成整改，验收组需复核。
-- **现场整改**：对监控管线接头脱落进行全面检查，保证有效性和安全性；对提升通道雨水倒灌问题考虑技术措施解决；对廊桥竖条加密，增加安全保障；对局部装饰装修损伤进行检查修补，并打扫卫生；对厂区排水系统进行最后清理和排查；对混凝土路面裂纹重新清理，用防水材料全部封闭。
-- **人员履约**：完善人员统计、护照和证件有效期等资料，人员统计需包含厂家服务人员。
-- **不可预见费**：验收组继续跟踪和完善不可预见费使用资料，确保依据证据和数据充分无误，后续专门对接。
-- **姆皮卡点验收**：会后及时安排剩余工作，注意交通安全和疫情防控。</t>
+- **核心交付物**：完成姆皮卡点现场验收，汇总三个厂区资料至卢萨卡分类成册，编制竣工图并组卷编码，形成最终验收报告。
+- **验收标准**：按合同、规章制度及援外项目执行手册管理办法，确保整改闭环，不留遗留未决事项。
+- **关键时间节点**：混凝土路面开裂整改最迟在出报告前完成，验收组复核；资料在验收完成第一时间汇总。
+- **资源协调**：管理组与技术组会后细化问题并制定方案，验收组负责追溯路面开裂问题，与相关单位专题研究。
+- **整改闭环要求**：现场实体整改编制方案逐一落实，人员履约资料完善，不可预见费使用资料跟踪完善。
+- *依赖前提*：姆皮卡点路途遥远、路况差，需注意交通安全与疫情防控。</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/2777</t>
+          <t>11110/2970</t>
         </is>
       </c>
     </row>
@@ -3404,113 +3383,102 @@
       <c r="C9" t="inlineStr">
         <is>
           <t># 发布会概况
-中金公司于周一召开宏观策略争论会议，由策略组分析师刘刚凯文主持，围绕大美丽法案、关税更新、港股流动性、反内卷与光伏、人形机器人、游戏板块等热点展开分析，并给出投资建议。会议指出，大美丽法案提高债务上限约5万美元，延长2017年减税法案（新增支出3.4万亿美元，每年3400亿），取消899条款；关税收入每年3000~4000亿美元可弥补支出，财政赤字率维持在5~6%。
-刘刚凯文认为，大美丽法案短期提振有限，但中长期从信用周期看有利；三季度流动性有波折，波动提供再配置机会，对美股美债不悲观。关税大概率是谈判技巧，市场静观其变，有效税率不会大幅提高，对通胀影响有限。港股流动性三季度不如二季度，但基本面强可盖过影响，建议低迷时介入，亢奋时锁定利润。
-公用事业风光首席分析师刘佳妮指出，光伏行业供需失衡严重，反内卷政策力度升级，硅料整合最迫切，电池环节供需最好。机械军工分析师郭文秀认为，人形机器人三季度关注华为链、本土企业技术闭环、特斯拉硬件替代窗口。传媒首席分析师张雪琴表示，游戏板块在消费、政策、新品周期三重利好下，有望在调整后再次实现戴维斯双击。
+中金公司策略组于周一召开宏观策略争论会议，由策略分析师刘刚凯文主持，围绕近期市场关注的大美丽法案、关税政策、港股流动性、反内卷光伏、人形机器人及游戏板块等热点展开分析，并给出投资建议。会议指出，大美丽法案提高债务上限约5万亿美元，延长2017年减税法案（新增支出3.4万亿美元，每年3400亿），取消899条款；关税收入每年约3000-4000亿，可弥补支出，财政赤字率维持在5-6%。会议整体基调为：大美丽法案对经济短期提振有限但中长期有利，三季度流动性有波折，波动提供再配置机会；关税大概率是谈判技巧，市场静观其变；港股流动性边际收紧但基本面强可盖过影响；光伏反内卷政策力度升级，价格恶性竞争有望告一段落；人形机器人三季度关注华为链、本土企业技术闭环、特斯拉硬件替代窗口；游戏板块在消费、政策、新品周期三重利好下，调整后有望再次实现戴维斯双击。
 # 核心信息
-- **大美丽法案三大块**：解决债务上限（提高约5万美元）、延长2017年减税法案（新增支出3.4万亿美元，每年3400亿）、取消899条款。
-- **债务上限影响**：提高后消除违约风险，可新增发债与支出；若假设GDP不增长，债务占GDP比例可能高达135%。
-- **减税法案延长**：避免2017年减税法案年底失效导致居民与企业税率大幅上升；需在现有高基数上多花3.4万亿美元，每年额外支出3400亿，同时削减其他支出（含减少新能源补贴1.4万亿美元）。
-- **取消899条款**：此前条款要求海外投资者购买美债时缴纳利息所得税，引发主权基金抛售美债担忧；取消后该风险消除，维护美元体系根基。
-- **关税收入对冲**：当前约10%以上税率每年带来关税收入3000~4000亿美元，可弥补每年3400亿额外支出，财政赤字率基本维持在5~6%，不会大幅增加。
-- **三季度抽水效应**：7~9月财政部需发债约1万亿美元并回补TGA账户，带来流动性供给压力；参照2023年三季度发债1万亿美元时，美债利率从3.8%升至5%，美股小幅下跌4~5%。
-- **期限溢价水平**：当前期限溢价已处于2013年以来高点，预计美债利率抬升幅度不会达到2023年水平（3.8%~5%）。
-- **信用周期框架**：美国经济如烧篝火可自然修复，上半年遭遇三盆冷水（1月DeepSeek冲击、财政收缩、4月2日对等关税）；中国经济如煮水需持续添柴，下半年美国环比改善、中国高基数下可能边际走弱。
-- **关税四点判断**：①一定会做（需支撑收入与支出）；②需维持一定税率（当前豁免10%水平即可收上3000~4000亿美元）；③不能太高（过高通胀受不了）；④市场逐渐脱敏，静观其变。
-- **关税新变化**：时间拖后（原7月9日达成）；相比4月2日对等关税水平大部分回落（除巴西）；加拿大、墨西哥、欧盟因贸易占比高被单拎出来，其他国家对有效税率影响很小（最高日本占比4.5%）。
-- **有效税率测算**：当前约10~12%；若8月1日关税全回去，可能回到10~15%，最极端18%；对通胀压力缓慢抬升，年底可能到3.3~3.4%。
-- **美联储降息判断**：7月降息勉强（关税仍有不确定性），9月后四季度可降息；即便有效税率18%也不大幅改变通胀路径。
-- **对华关税与转口限制**：对华关税约40~50%（2018年约20%为基数）；越南、英国达成协议含转口限制（越南转口限制40%），需关注8月12日中美谈判进展及转口限制。
-- **港股流动性**：7~9月美债利率走高、美元流动性供给压力，美元四季度可能小幅走强，边际挤压港股；但美元美债利率并非港股唯一变量，基本面强可盖过影响。
-- **港股微观流动性**：5月后HIBOR大幅下降（金管局投放大量资金），港币触及7.85；金管局可小幅收紧（如收90亿、放1000多亿）延缓利率收紧速度，但边际上流动性相比二季度变紧；IPO融资较多也形成约束。
-- **港股点位与风格**：恒指在23000~24000区间震荡；建议低迷时积极介入、亢奋时适度锁定利润；长期方向两头分红（银行短期溢价低于20%，股息率扣税后优势不大；1.25%仍是隐形底），成长端关注新消费（拥挤）、创新药（稍降）、科技硬件与AI应用（相比3月降幅大，可提前布局）。
-- **光伏行业供需失衡**：全球新增光伏装机从2020年130GW升至2024年530GW（4年CAGR 42%）；预计2025~26年全球光伏需求增速回落至10%左右；2025年全球需求650~700GW，电池产能是需求1.5倍、硅片组件2倍、硅料2.5倍。
-- **光伏价格与亏损**：2022年以来产业链价格下跌70%~90%；硅片电池自2023年四季度亏损，硅料组件自2024年二季度正式亏损；持续亏损下尚未看到改变供需格局的企业退出。
-- **反内卷政策时间线**：2024年5月17日光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会（强调市场化手段+政府有形手）；2025年2月国常会提出化解重点产业结构性矛盾；6月29日起连续5天上层三次发声（人民日报发文指出光伏高投入低产出、阶段性供需错配、政绩观错位等问题）；7月1日总书记主持中财委第6次会议提出依法依规治理低价无序竞争、推动落后产能退出；7月3日工信部召开光伏企业座谈会（指出技术创新、产业产能升级是重要手段）。
-- **硅料环节整合最迫切**：集中度高（在产企业不到20家）；成本曲线陡峭（颗粒硅现金成本约28元/公斤，尾部国内厂商高达45元/公斤，当前丰水期行业边际现金成本约38元/公斤）；供需比超200%，高于其他环节150%左右；作为最上游影响全产业链定价。
-- **电池环节供需最好**：PERC电池资产（约500GW）基本退出市场，TOPCon占90%市场份额，BC技术渗透率提升至单月5~6%。
-- **光伏玻璃产能出清**：2024年9月第一轮产能出清（有效产能降幅约6%）；第二轮协会呼吁降产保价，参加企业计划7月开始降产30%；需出清约2万吨方可修复供需平衡；当前价格已创历史新低，龙头企业经营性成本约1元/平方米，后续不排除亏损幅度加大。
-- **光伏市场反馈**：多晶硅期货价格上周触及40元/公斤（前一周约35元），现货报价大幅上涨；硅片报价上涨约10%，电池上涨约2分钱；过去两周硅料和玻璃股价上涨20~30%，组件涨幅约10%（受136号文新能源全面入市政策影响，下游电站对价格传导接受度待观望）。
-- **光伏企业穿越周期能力**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流，财务压力小于上游；低杠杆、强现金、强融资能力企业（部分资产负债率仅10%出头）财务健康度优于同行；技术创新持续（颗粒硅使用比例从10~20%提升至50%、硅片薄片化、钨丝导入、浆料铜替代银2025~26年大规模导入、TOPCon取代PERC）。
-- **人形机器人二季度表现**：A股机器人板块4~6月按流通市值加权平均跌幅约9%，跑输机械设备约12个百分点；特斯拉核心供应商标签股从3月高点普遍回调30%~40%；5~6月交易型资金止损明显。
-- **人形机器人回调原因**：特斯拉4月后宣布量产时间线后移，叠加中美关税情况，降低A股风险偏好；标签股难创新高，资金涌向小盘/微盘呈现扩散行情。
-- **华为具身智能平台**：6月底华为发布CloudRobot具身智能平台，标志云边端一体化计算架构成国内市场潮流；盘古世界模型首发，支持点云和视频双模态同时生成，解决训练物理模型痛点；CloudRobot构建三大能力（多模态生成模型提供泛化训练环境、规划大模型支持自主决策、执行大模型将操作精度提升至毫米级）。
-- **华为商业模式**：明确不造机器人，以RTC方式向全社会开放，有望探索AI agent或license收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作。
-- **本土人形机器人企业进展**：智元机器人企图通过收购控股材料厂商在A股上市（具备AI+双足及轮式全栈能力），相关零部件厂商股价出现底部异动；宇树科技年收入突破10亿元，下半年有望加速上市；智元、宇树同时中标中国移动旗下接近1.2亿元人形机器人采购订单（部署于移动营业厅与消费者互动）。
-- **人形机器人投资场景**：国内至少100家以上本体厂商；优先关注投资回报率明确的场景，重点提示物流端（降低单件运输成本是2025年下游客户明确刚需）。
-- **特斯拉硬件瓶颈与替代窗口**：Optimus存在电机过热、灵巧手负载不足、续航问题，特斯拉正在变更方案并筛选供应商；电机过热对应无框力矩电机新品（改善散热性能），续航问题对应轻量化方向（以塑代钢、替代铝合金）。
-- **港股机器人板块**：二季度呈现明显估值溢价（PE、PS均显著），源于流动性红利及进入港股通/相关指数后享受全球科技资金关注；下半年有确定性扩容，可关注A+H动向。
-- **人形机器人三季度关注信号**：①华为云生态接入厂商三季度继续新增；②头部企业出货量跨越年化500台或1000台；③聚焦零部件、电机硬件优化窗口；技术创新、产业需求、工厂替代三重周期共振时孕育投资机会。
-- **游戏板块近期表现**：上涨接近两三个月，上周末开始调整；6月24日起半个月涨幅最猛烈；观点仍看好。
-- **游戏政策支持**：今年1月和3月国务院层面对传媒板块发布游戏行业支持政策；广东、浙江、北京、上海等地出台专门政策支持包（含中小微企业奖励、出海支持、IP方向）；政策支持力度达空前高度。
-- **版号发放常态化**：今年每月可同时发放国产和进口网络游戏版号；6月单月发放158个（国产147个、进口11个），为2018年以来单月最高水平；版号从研发到上线不再是障碍，而是正常审批流程。
-- **游戏市场规模**：2024年8月以来游戏市场单月持续正增长；今年1~5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%。
-- **游戏新品周期**：今年缺乏大厂大作（腾讯、网易重点产品相对少，米哈游无重磅作品），但中型厂商新品亮眼：吉比特《仗剑传说》5~6月上线首月流水2亿多；巨人网络《超自然行动组》6月流水过亿，年化乐观约20亿元量级，利润提升50%以上；中型厂商获客ROI良好，新品成为A股及港股中型公司核心催化。
-- **游戏估值水平**：TTM PE约30倍（2023年AI行情到过45倍）；2025年静态PE约20倍，明年更低；游戏板块具逆周期性（悦己型消费，1~5月同比增长17%），政策支持，新品周期延续。
-- **游戏利润滞后性**：新品存在前期买量成本投入与流水递延确认的后置差异，今年上新品的利润更多明年兑现；建议关注新品市场表现、用户获取下载榜排名等领先指标；板块估值提升仍有空间，有望实现戴维斯双击。
+- **大美丽法案三大块**：解决债务上限（提高约**5万亿美元**）、延长2017年减税法案（新增支出**3.4万亿美元**，每年额外支出**3400亿**）、取消`899条款`；债务上限提高后违约风险消除，但若假设GDP不增长，债务占GDP比例可达**135%**。
+- **减税法案性质**：非新增减税，主要是延长2017年已有减税法案，若不延长今年底将出现大幅加税；延长需在现有高基数上多花**3.4万亿美元**，每年**3400亿**，若无收入弥补将转化为债务；同时减少其他支出（含新能源补贴）**1.4万亿美元**。
+- **取消899条款**：此前主权基金及海外投资者购买美债需缴利息所得税，取消后避免其抛售美债，维护美元体系根基。
+- **财政赤字测算**：当前约**10%多**的关税税率每年带来关税收入**3000–4000亿**，可弥补每年**3400亿**新增支出，财政赤字率基本维持在**5–6%**，不会大幅增加。
+- **三季度流动性冲击**：7–9月财政部需发债约**1万亿美元**并回补TGA账户，带来额外供给；参考2023年三季度发债1万亿推高美债利率从**3.8%升至5%**、美元走强、美股下跌约**4–5%**；本次期限溢价已处于**2013年以来高位**，利率抬升幅度可能不及2023年。
+- **信用周期判断**：美国经济环比改善（低基数），中国面临高基数，边际上此消彼长；判断四季度美元可能小幅走强、美股可能反弹跑赢。
+- **关税四点信息**：① 一定会做（支撑收入）；② 需维持一定税率（当前豁免10%水平可收上**3000–4000亿**）；③ 不能太高（通胀受不了）；④ 市场逐渐脱敏。
+- **关税新变化**：时间拖后（原7月9日）；大部分国家税率相比4月2日对等关税水平回落（巴西除外）；加拿大、墨西哥、欧盟贸易占比高需重点谈判，日本占比仅**4.5%**，其他国家对有效税率影响小。
+- **有效税率测算**：当前**10–12%**；若8月1日关税全回去，可能回到**10–15%**，最极端**18%**；通胀压力缓慢抬升，年底可能升至**3.3–3.4%**。
+- **美联储降息判断**：7月降息勉强（关税有不确定性），9月及四季度之后仍可降息；即便有效税率达18%也不大幅改变通胀路径。
+- **对华关税与转口限制**：对华关税约**40–50%**（2018年约20%）；越南达成协议含**40%**转口限制，英国协议亦有转口限制；需关注**8月12日**中美谈判进展及转口限制。
+- **港股流动性**：7–9月美债利率走高、美元流动性供给压力，边际上略偏负面；港股5月后HIBOR大幅下降（金管局投放大量资金），港币汇率在**7.84–7.85**，金管局需收紧流动性但可小幅收（如收90亿、放1000多亿）；三季度流动性供给不如二季度，IPO融资亦形成约束。
+- **港股点位与风格**：恒指在**23000–24000**区间震荡；港股内部极致分化，结构性行情集中在AI互联网、创新药、新消费等；银行股溢价已低于**20%**（除保险外股息率扣税后无优势），短期透支但长期仍有空间。
+- **光伏供需失衡**：全球新增光伏装机从2020年**130GW**增至2024年**530GW**（CAGR **42%**）；预计2025–26年全球光伏需求增速回落至**10%**左右；2025年全球需求预计**650–700GW**，电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**。
+- **光伏价格与亏损**：2022年以来产业链价格下跌**70%–90%**；硅片电池自2023年四季度亏损，硅料组件自2024年二季度正式亏损；目前未见改变供需格局的企业退出。
+- **反内卷政策时间线**：`2024年5月17日`光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会；`2025年2月`国常会提出化解重点产业结构性矛盾；`6月29日`起连续5天人民日报发声（指出光伏高投入低产出、阶段性供需错配、政绩观错位等问题）；`7月1日`中财委第6次会议提出依法依规治理低价无序竞争、推动落后产能退出；`7月3日`工信部召开光伏企业座谈会，指出技术创新与产能升级是反内卷重要手段。
+- **硅料环节整合最迫切**：集中度最高（在产企业不到20家）、成本曲线最陡峭、供需比超**200%**；当前丰水期硅料边际现金成本约**38元/公斤**，颗粒硅现金成本约**28元/公斤**，尾部厂商现金成本高达**45元/公斤**。
+- **电池环节供需最好**：PERC电池约**500GW**资产基本退出市场，TOPCon占**90%**市场份额，BC技术单月渗透率提升至**5–6%**。
+- **光伏玻璃产能出清**：2024年9月第一波产能出清（有效产能降幅约**6%**）；当前协会呼吁降产保价，企业计划7月起降产**30%**；需出清约**2万吨**方可修复供需平衡；价格已创历史新低，龙头企业经营性成本约**1元/平米**。
+- **光伏价格反弹**：多晶硅期货价格上周触及**40元/公斤**（前一周现货约**35元**）；硅片报价涨约**10%**，电池涨约**2分钱**，组件涨幅靠后约**10%**；过去两周硅料和玻璃股价上涨**20–30%**。
+- **光伏企业穿越周期能力**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流；部分企业资产负债率仅**10%出头**；技术变革包括颗粒硅使用比例从**10–20%提升至50%**、硅片薄片化、铜替代银（2025–26年大规模导入）。
+- **人形机器人二季度表现**：A股机器人板块按流通市值加权平均跌幅约**9%**，跑输机械设备板块约**12个百分点**；特斯拉核心供应商标签股从3月高点普遍回调**30%–40%**；回调主因是特斯拉4月后宣布量产时间线延后、叠加中美关税影响风险偏好。
+- **华为云具身智能平台**：6月底华为开发者大会首发`盘古世界模型`，支持点云和视频双模态同时生成；`CloudRobot`平台构建三大能力：多模态生成模型（泛化训练环境）、规划大模型（自主决策）、执行大模型（操作精度提升至**毫米级**）；华为明确不造机器人，以RTC方式开放，探索AI agent或license收费。
+- **本土人形机器人企业进展**：智元机器人拟通过收购材料厂商在A股上市，具备AI+双足、轮式全栈能力；宇树科技年收入突破**10亿元**，下半年有望加速上市；智元、宇树同时中标中国移动旗下接近**1.2亿元**人形机器人采购订单（部署于移动营业厅）。
+- **特斯拉硬件瓶颈**：Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案并筛选供应商；国内人形机器人本体厂商至少**100家以上**。
+- **港股机器人板块**：二季度估值溢价明显（PE、PS均高），源于稀缺性和流动性红利；下半年有确定性扩容，可关注A+H动向。
+- **游戏板块政策支持**：国务院1月和3月发布游戏行业支持政策；广东、浙江、北京、上海等地有专门政策支持包（含中小微企业奖励、出海支持、IP方向）。
+- **版号发放**：今年6月单月发放**158个**（国产**147个**、进口**11个**），为**2018年以来单月最高**；自去年四季度起每月正常发放国产及进口版号。
+- **游戏市场规模**：2024年8月以来单月持续正增长；今年1–5月游戏市场规模同比增长**17%**（**1400多亿**），手游同比增长**20%**。
+- **游戏新品表现**：吉比特《仗剑传说》5–6月上线，首月流水**2亿多**；巨人网络《超自然行动组》6月流水过亿，年化约**20亿元**量级，利润提升**50%以上**；大厂缺少大体量产品，中型厂商获客友好、ROI良好。
+- **游戏板块估值**：TTM PE约**30倍**（2023年AI行情到过**45倍**）；2025年静态PE约**20倍**；新品利润有滞后性，更多在明年兑现。
 # 官方表态
-中金公司宏观策略组分析师刘刚凯文在本次会议上，就大美丽法案、关税、港股流动性等宏观议题主动阐述观点，并给出投资建议。
-- **大美丽法案定性**：该法案不能严格意义上称为减税法案，因没有新增减税，大部分是延长2017年已有的减税法案；若不延长，今年底将出现大幅加税，对居民收入、消费和经济有明显影响。
-- **债务上限与财政**：债务上限提高约5万美元，消除了违约风险，使其可以花钱；若简单假设GDP不增长，债务占GDP比例可能高达135%；新增支出3.4万亿美元（每年3400亿），但关税收入每年约3000~4000亿美元可弥补，财政赤字率基本维持在5~6%，不会大幅增加。
-- **取消899条款**：899条款即购买美债需对利息所得征税，取消后主权基金和海外投资者不会因该条款抛售美债，维护了美元体系根基。
-- **信用周期判断**：美国经济像烧一团篝火，不泼冷水会慢慢缓过劲；中国经济像煮一壶水，需持续添柴，添柴速度变慢水温会降；上半年美国遭遇三盆冷水（1月DeepSeek、财政收缩、4月2日对等关税），下半年环比可能改善。
-- **美股美债态度**：对美股美债不悲观，三季度有流动性波折需过坎，波动提供再配置机会；美债利率近期往上蹭，但不必然导致大跌，若担心估值高可以等一等，不赌这个事。
-- **关税四点信息**：第一，关税一定要做，用来支撑收入和支出；第二，需维持一定税率（当前豁免10%的水平）才能收上来3000~4000亿；第三，不能太高，太高通胀受不了；第四，市场逐渐脱敏，静观其变。
-- **关税新变化**：时间变相拖后（原7月9日达成）；相比4月2日对等关税水平大部分回落（除巴西）；加拿大、墨西哥、欧盟因贸易占比高被单拎出来，其他占比几乎可忽略；有效税率当前约10~12%，若8月1日全回去可能回到10~15%，最极端18%。
-- **关税对通胀与降息**：通胀压力会缓慢抬升，年底约3.3~3.4%；美联储7月降息很勉强，9月及四季度之后可以降，即便18%的有效税率也不大幅改变通胀路径。
-- **对华关税关注点**：对华关税约40~50%（2018年姑且算20%）；越南、英国达成的协议都有转口限制，越南转口限制40%，比我们对华税率还低；需关注8月12日中美谈判进展及转口限制。
-- **港股流动性判断**：7~9月美债利率走高、美元流动性有供给压力，美元四季度可能小幅走强，边际上对港股略微偏负面；但美元美债利率不是绝对主导港股市场的唯一变量，自身基本面强完全可以盖过影响。
-- **港股微观流动性**：5月后HIBOR大幅下降，金管局投放大量资金，流动性强但港币触及7.85；金管局不能决定要不要收、何时收，但能决定怎么守，连系汇率制度一定是最优先考虑，一定会收，但可小幅收（如收90亿、放1000多亿）延缓利率收紧速度；边际上流动性相比二季度一定变紧，三季度流动性供给不如二季度，IPO融资也形成约束。
-- **港股风格建议**：长期方向还是两头分红，但银行股溢价已低于20%，除保险外其他投资者买港股银行股扣税后股息率无太大优势，短期有点透支；短期125%还是隐形底；成长端新消费较拥挤，创新药稍降，科技硬件、AI应用相比3月降下来非常多，反而提供提前埋伏、提前布局的策略；中期创新药、人形机器人、AI应用、短视频生成、软件可能逐渐有催化剂。
-- **投资总原则**：在合适的位置拿长期正确的板块，低迷时积极介入，亢奋时适度锁定利润。
-刘佳妮（中金公司公用事业风光公用事业首席分析师）就光伏反内卷表态：
-- **反内卷必要性**：2022年以来产业链价格下跌70%~90%，硅片电池自2023年四季度亏损，硅料组件自2024年二季度正式亏损；持续亏损下尚未看到改变供需格局的企业退出，未来两年全球需求增速回落至10%左右，无法消化目前产能，因此期待政府干预，认为有一定必要性。
-- **政策级别提升**：2025年反内卷力度和政策级别进一步提升——2月国常会提到化解重点产业结构性矛盾；6月29日起连续5天上层发生三次发声（人民日报《在破除内卷式竞争中实现高质量发展》指出光伏高投入低产出、阶段性供需错配、高标准市场体系尚待健全、部分地方政绩观错位等问题）；7月1日总书记主持召开中财委第6次会议提到依法依规治理企业低价无序竞争、引导产品品质、推动落后产能退出；7月3日工信部再度召开光伏企业座谈会，指出技术创新、产业产能升级是光伏反内卷的重要手段。
-- **硅料整合最迫切**：硅料环节集中度高（在产企业不到20家）、成本曲线最陡峭（颗粒硅现金成本约28元/公斤，尾部国内厂商高达45元/公斤）、供需比超200%高于其他环节150%左右，且作为最上游影响整个产业链定价，因此整合最为迫切。
-- **电池环节供需最好**：约500GW的PERC电池资产已基本退出市场，TOPCon占据90%市场份额，BC技术渗透率单月已提升至5~6%，供需情况最为良好。
-- **光伏玻璃产能出清**：2024年9月经历第一波产能出清，有效产能降幅约6%；当前协会呼吁降产保价，企业自发开始第二轮产能出清，参加企业计划7月开始降产30%；测算国内光伏玻璃产能需出清约2万吨方可修复供需平衡；当前价格下龙头企业经营性成本已是一元每平方，后续不排除亏损幅度进一步加大。
-- **市场反馈**：官媒发声、中财委会议及工信部座谈会后，多晶硅期货价格大幅反弹，截至上周五触及40元/公斤；现货价格较前一周35元左右大幅上涨；硅片报价上涨约10%，电池上涨约两分钱；过去两周硅料和玻璃股价上涨20~30%，组件环节涨幅相对靠后约10%。
-- **穿越周期企业特征**：头部一体化组件企业可通过收现款再发货、占用上游供应商账期获得正向经营现金流，财务压力相对小于上游环节；低杠杆、强现金、强融资能力的企业财务健康程度显著优于同行；技术创新和成本竞争能力是行业不变主旋律，颗粒硅使用比例从10~20%提升到50%，硅片薄片化、细线化、钨丝全面导入，电池浆料铜替代银将在2025~26年大规模导入，TOPCon从2022~24年逐步取代PERC。
-- **政策效果预期**：随着反内卷力度不断强化升级，价格恶性竞争有望告一段落，至少对行业来讲夯实了底部。
-郭文秀（中金公司机械军工分析师）就人形机器人表态：
+**中金公司策略组**（刘刚凯文）就大美丽法案、关税与港股流动性作宏观策略表态：
+- **大美丽法案定性**：不能严格意义上称为减税法案，因没有新增减税，大部分是延长2017年已有减税法案；不延长则今年底会出现大幅加税，对居民收入、消费和经济有明显影响。
+- **债务上限**：提高约5万亿美元，至少使违约风险消除、政府可以花钱；若简单假设GDP不增长，债务占GDP比例可能高到135%。
+- **财政支出与赤字**：延长减税需在现有高基数上多花3.4万亿美元，每年额外支出3400亿；同时减少其他支出（含新能源补贴）1.4万亿；关税收入每年约3000–4000亿可弥补支出，财政赤字率基本维持在5–6%，不会大幅增加。
+- **取消899条款**：该条款对美债利息所得征税，导致主权基金和海外投资者不持有美债；取消后大概率不可能用此方式收钱，避免影响美国美元体系根基。
+- **三季度流动性判断**：7–9月财政部需发债约1万亿美元回补TGA账户，带来额外供给；参照2023年三季度发债1万亿推高美债利率从3.8%升至5%、美股小幅下跌4–5%，本次期限溢价已处于2013年以来高位，利率可能到不了5%以上。
+- **对美股美债态度**：重申并不悲观，波动提供再配置机会；但涨到这个位置预期打得比较多，再往里冲性价比不高，若出现波动依然是再配置机会。
+- **关税四点判断**：第一，关税一定要做，用来支撑收入与支出；第二，需维持一定税率才能收上钱，现在豁免10%的水平即可收3000–4000亿；第三，不能太高，太高通胀受不了；第四，市场逐渐脱敏、静观其变。
+- **关税新变化**：时间变相拖后（原7月9日）；相比4月2日对等关税水平大部分回落（除巴西外）；加拿大、墨西哥、欧盟贸易占比高需谈妥，其他国家即便增加一倍也不影响有效税率（日本占比仅4.5%）。
+- **有效税率测算**：当前约10–12%；若8月1日全回去甚至更高，大不了回到10–15%，最极端回到18%；通胀压力缓慢抬升，年底约3.3–3.4%，即便18%也不大幅改变通胀路径。
+- **美联储降息判断**：7月降息很勉强，因关税仍有不确定性；9月及四季度之后还是可以降。
+- **对华关税与转口限制**：对华关税约40–50%；越南达成协议有40%转口限制，比我们税率还低，需密切关注8月12日中美谈判进展及转口限制。
+- **港股流动性**：7–9月美债利率走高、美元流动性供给压力，加上港币在7.84–7.85、金管局需收紧流动性，三季度流动性供给不如二季度；但美元美债利率不是绝对主导港股市场的唯一变量，自身基本面强完全可以盖过影响。
+- **港股风格建议**：长期方向还是两头分红，但银行股溢价已低于20%，除保险外其他投资者买港股银行股扣税后股息率已无太大优势，短期有点透支；短期125%还是隐形底；成长端新消费较拥挤、创新药稍降，科技硬件和AI应用相比3月已降下来非常多，反而提供提前埋伏机会。
+**中金公司公用事业风光首席分析师刘佳妮**就光伏反内卷表态：
+- **反内卷必要性**：2022年以来产业链价格下跌70%–90%，硅片电池自2023年四季度亏损、硅料组件自2024年二季度正式亏损，但持续亏损下尚未看到改变供需格局的企业退出，未来两年全球需求增速回落至10%左右、无法消化目前产能，因此期待政府干预、认为有一定必要性。
+- **政策升级判断**：2024年更多是行业协会主导，2025年政策级别进一步提升——2月国常会提出化解重点产业结构性矛盾，6月29日起人民日报连续发声指出光伏高投入低产出、阶段性供需错配、高标准市场体系尚待健全、部分地方政绩观错位等问题，7月1日中财委第六次会议提出依法依规治理企业低价无序竞争、引导产品品质、推动落后产能退出，7月3日工信部再度召开光伏企业座谈会传达产业重要性与破除反内卷迫切性。
+- **硅料整合最迫切**：集中度在四个环节中最高（在产企业不到20家）、成本曲线最陡峭（颗粒硅现金成本约28元/公斤，尾部国内厂商高达45元/公斤）、供需比超200%高于其他环节150%左右，且作为最上游影响整个产业链定价。
+- **电池环节供需最好**：PERC电池资产约500GW已基本退出市场，TOPCon占据90%市场份额，BC技术单月渗透率已提升至5–6%。
+- **光伏玻璃第二轮出清**：2024年9月第一波产能出清有效产能降幅约6%；当前协会呼吁降产保价，企业计划7月起降产30%，测算需出清约2万吨方可修复供需平衡；价格已创历史新低，龙头企业经营性成本约1元/平米，后续不排除亏损幅度进一步加大。
+- **价格与市场反馈**：多晶硅期货价格已触及40元/公斤，现货报价较前一周35元左右大幅上涨，硅料市场呈现触底企稳态势；硅片报价涨约10%、电池涨约2分钱、组件涨幅靠后约10%；过去两周硅料和玻璃股价上涨20–30%。
+- **组件价格传导需观望**：组件有跟涨意愿，但下游电站受136号文（新能源全面入市）影响电价不确定性大幅增加，能否接受产业链价格上涨传导还需观望未来一段时间招标情况。
+- **穿越周期企业特征**：头部一体化组件企业可通过收现款再发货、占用上游供应商账期获得正向经营现金流，财务压力相对小于上游；部分企业资产负债率仅10%出头、2023–24年资本开支谨慎；持续亏损加速降本增效——颗粒硅使用比例从10–20%提升至50%、硅片薄片化、铜替代银将在2025–26年大规模导入。
+**中金公司机械军工分析师郭文秀**就人形机器人三季度趋势表态：
 - **三季度三大主线**：华为云生态开放、本土人形机器人企业技术闭环、特斯拉延期带来的硬件替代窗口期。
-- **华为链技术突破**：6月底华为开发者大会首发盘古世界模型，通过时空可控生成技术实现2D视频模态和3D激光点云模态像素级对应，是首个支持点云和视频双模态同时生成的大模型；CloudRobot平台构建三大基础能力——多模态生成模型提供泛化训练环境、规划大模型帮助自主决策、执行大模型将操作精度提升到毫米级。
-- **华为商业模式**：华为明确强调不造机器人，以RTC方式向全社会开放，有望探索类似AI agent收费或license收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作，云智能加场景深耕模式有望下半年看到更多。
-- **本土企业资本运作**：智元机器人企图通过收购控股材料厂商在A股上市，具备AI+双足及轮式人形机器人全栈能力，相关零部件厂商股价出现明显底部异动；宇树科技公开表示年收入已突破10亿元，下半年有望加速上市。
-- **商业落地场景**：智元、宇树两家企业同时中标中国移动旗下接近1.2亿元人形机器人采购订单，有望部署在移动营业厅与消费者互动；建议优先关注投资回报率明确的场景，重点提示物流端——降低单件运输成本是2025年下游客户明确刚需。
-- **特斯拉延期与硬件瓶颈**：Optimus存在电机过热、灵巧手负载不足、续航问题等硬件问题，特斯拉在变更方案、筛选供应商；这些硬件瓶颈也是人形机器人共性瓶颈，电机过热对应无框力矩电机散热改善，续航问题对应以塑代钢等轻量化方向。
-- **港股机器人板块**：二季度港股机器人板块估值溢价明显（无论PE还是PS），源于流动性和进入港股通后享受全球科技资金关注；下半年港股机器人板块有确定性扩容，可关注A+H相关动向。
-- **三季度关注三类信号**：华为云生态接入厂商继续新增的趋势；头部企业出货量跨越年化500台或1000台背后的股价及供应商演绎机会；聚焦电机硬件优化对应的窗口期。
-张雪琴（中金公司传媒行业首席分析师）就游戏板块表态：
-- **政策端友好度空前**：去年《黑神话：悟空》爆火后游戏行业文化价值和经济价值得到广泛认可，政府政策支持力度达到空前高度；今年1月和3月国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地有专门政策支持包，包括中小微企业奖励、数字内容文化产业出海支持、IP等方向。
-- **版号发放常态化**：从去年四季度以来版号发放每月节奏良好，今年已进化到每月既可发国产也可发进口网络游戏版号；6月单月发放158个（国产147个、进口11个），是2018年以来单月最高水平，版号不再是障碍而是正常审批流程。
-- **市场增长数据**：2024年8月以来游戏市场单月持续正增长；今年1~5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%。
-- **新品周期判断**：年初市场普遍认为今年缺乏产品大作（腾讯、网易、米哈游均无特别重磅作品），但中型厂商新品亮眼——吉比特《仗剑传说》6月上线首月流水2亿多，巨人网络《超自然行动组》6月流水过亿、年化乐观看20亿元量级、利润提升50%以上；大厂缺少大体量产品对中型厂商获客友好，国内大多数新游获客ROI非常OK。
-- **估值与展望**：TTM PE约30倍（2023年AI行情到过45倍），2025年静态PE约20倍、明年更低；游戏板块当下与两年前不同——是悦己型消费领域、不受宏观经济影响、逆周期性，政策与两年前完全不同，新品周期还在延续（三七《斗罗》上周五上线，网易腾讯新品更多落在明年大周期）。
-- **利润滞后性提醒**：新品存在前期用户获客买量成本投入和流水递延确认的后置差异，今年上新品更多利润要明年兑现；表观今年估值20来倍不便宜，但对明年业绩确定性提供坚实基础。
-- **跟踪指标建议**：关注新品市场表现、用户获取下载榜排名等指标，流水是领先指标，利润相对滞后；短期板块估值提升还有较大空间，市场对利润预期有一定修正增长，最后实现戴维斯双击。
-- **结论**：在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击。
+- **华为链技术突破**：6月底华为开发者大会首发盘古世界模型，通过时空可控生成技术实现2D视频模态与3D激光点云模态像素级对应，首个支持点云和视频双模态同时生成；CloudRobot平台构建多模态生成模型、规划大模型、执行大模型（操作精度提升到毫米级）三大能力。
+- **华为商业模式**：明确强调不造机器人，以RTC方式向全社会开放，未来有望探索类似AI agent收费或license收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作，云智能加场景深耕模式有望下半年看到更多。
+- **本土企业资本运作**：智元机器人拟通过收购方式控股材料厂商在A股上市，具备AI+双足及轮式人形机器人全栈能力；宇树科技年收入已突破10亿，下半年有望加速上市；智元与宇树同时中标中国移动旗下近1.2亿人形机器人采购订单，有望部署在移动营业厅与消费者互动。
+- **特斯拉延期与硬件窗口**：Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案、筛选供应商；这些硬件瓶颈也是国内人形机器人共性瓶颈——电机过热对应无框力矩电机散热改善新品，续航问题对应以塑代钢等轻量化方向。
+- **港股机器人板块**：二季度呈现明显估值溢价（无论PE还是PS），来自流动性红利与进入港股通后享受全球科技型资金关注；下半年有确定性扩容，可关注A+H相关动向。
+- **三季度关注三类信号**：华为云生态接入厂商三季度继续新增；头部企业出货量跨越年化500台或1000台背后的股价演绎；聚焦电机硬件优化对应的窗口期。
+**中金公司传媒行业首席分析师张雪琴**就游戏板块表态：
+- **政策友好度空前**：从去年《黑神话：悟空》爆火后游戏行业文化价值和经济价值得到广泛认可，政府支持力度达空前高度；今年1月和3月国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地有专门政策支持包，包括中小微企业奖励、数字内容文化产业出海支持、IP方向等。
+- **版号发放常态化**：今年已进化到每月既可发国产网络游戏版号也可发进口版号；6月单月发放158个（国产147个、进口11个），为2018年以来单月最高水平，版号从研发到上线不再是障碍而是正常审批流程。
+- **市场数据**：2024年8月以来游戏市场单月持续正增长；今年1–5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%。
+- **新品周期判断**：年初市场普遍认为今年缺乏产品大作（腾讯、网易及未上市的米哈游均无特别重磅作品），但中型厂商新品成为A股及港股中型公司核心催化——吉比特《仗剑传说》首月流水2亿多，巨人网络《超自然行动组》6月流水过亿、年化乐观约20亿量级、利润提升50%以上；大厂缺少大体量产品对中型厂商获客友好，国内大多数新游获客ROI非常OK。
+- **估值判断**：TTM PE约30倍（2023年AI行情到过45倍），2025年静态PE约20倍、明年更低；但游戏板块与两年前不同——定义在当前消费趋势下悦己型消费领域、不受宏观经济影响，政策与两年前完全不一样，新品周期还在延续。
+- **利润滞后提示**：新品存在前期用户获客买量成本投入与流水递延确认的后置差异，今年上新品利润更多滞后到明年兑现；表观今年估值20来倍不便宜，但为明年业绩确定性提供坚实基础。
+- **跟踪建议**：关注新品市场表现、用户获取下载榜排名等领先指标；短期板块估值提升还有较大空间，市场对利润预期有一定修正后实现整体戴维斯双击。
 # Q&amp;A环节
-**1. 记者（人民日报 张宇）**：大美丽法案对美元流动性、美债利率和美股的影响如何？三季度是否存在风险？
-**刘刚凯文**：大美丽法案提高债务上限约5万美元，延长2017年减税法案（新增支出3.4万亿美元，每年3400亿），取消899条款。关税收入每年3000~4000亿美元可弥补支出，财政赤字率维持在5~6%。7~9月有抽水效应，预计发债1万亿美元，类似2023年三季度，当时推高美债利率从3.8%至5%，美股小幅下跌4~5%。但期限溢价已处于2013年以来高点，美债利率可能不会像2023年那样大幅抬升。波动提供再配置机会，对美股美债不悲观。
-**2. 记者（新华社 李华）**：关税谈判的最新进展如何？对通胀和美联储降息有何影响？
-**刘刚凯文**：关税四点信息：一定会做、需维持一定税率（当前豁免10%水平）、不能太高、市场逐渐脱敏。新变化：时间拖后（原7月9日达成）、相比4月2日对等关税大部分回落（除巴西）、加拿大墨西哥欧盟单拎出来（贸易占比高）。有效税率当前10~12%，若8月1日全回去，可能回到10~15%，最极端18%。通胀压力缓慢抬升，年底可能到3.3~3.4%。美联储7月降息勉强，9月后可能降息。
-**3. 记者（财新 王芳）**：港股流动性三季度会如何变化？对港股市场有何影响？
-**刘刚凯文**：7~9月美债利率走高、美元流动性供给压力，美元四季度可能小幅走强，边际挤压港股。港股5月后微观流动性释放，HIBOR大幅下降，金管局投放大量资金。港币触及7.85，金管局需收紧流动性，但可小幅收（如收90亿，放1000多亿）。三季度流动性供给不如二季度，IPO融资也形成约束。恒指在23000~24000区间震荡。但基本面强可盖过流动性影响，建议低迷时介入，亢奋时锁定利润。
-**4. 记者（证券时报 陈明）**：光伏反内卷政策对行业各环节的影响如何？哪些环节最受益？
-**刘佳妮**：反内卷政策力度升级，硅料整合最迫切：集中度高（在产企业不到20家）、成本曲线陡峭（颗粒硅28元/公斤，尾部45元/公斤）、供需比超200%。电池环节供需最好：PERC退出，TOPCon占90%份额，BC渗透率5~6%。光伏玻璃2024年9月第一轮产能出清（降6%），第二轮计划7月降产30%，需出清约2万吨。多晶硅期货价格上周触及40元/公斤，现货价格较前一周35元大幅上涨。头部一体化组件企业穿越周期能力较强。
-**5. 记者（第一财经 刘洋）**：人形机器人三季度有哪些催化剂？投资主线是什么？
-**郭文秀**：三季度三大主线：华为链、本土企业技术闭环、特斯拉硬件替代窗口。华为6月底发布CloudRobot具身智能平台，盘古世界模型支持点云和视频双模态生成，三大能力（多模态生成、规划大模型、执行大模型）操作精度达毫米级。智元机器人企图通过收购控股材料厂商在A股上市，宇树科技年收入突破10亿元，两家同时中标中国移动近1.2亿元采购订单。特斯拉因电机过热、灵巧手负载不足、续航问题延期，带来硬件替代窗口。
-**6. 记者（上海证券报 赵敏）**：游戏板块近期调整后，估值是否还有提升空间？新品周期能否延续？
-**张雪琴**：游戏板块上涨接近两三个月，上周末开始调整，观点仍看好。6月单月版号发放158个（国产147个，进口11个），2018年以来单月最高。今年1~5月游戏市场规模同比增长17%，手游同比增长20%。TTM PE约30倍，2023年AI行情到过45倍；2025年静态PE约20倍。中型厂商新品亮眼：吉比特《仗剑传说》首月流水2亿多，巨人网络《超自然行动组》6月流水过亿，年化20亿量级，利润提升50%以上。新品利润有滞后性，今年新品利润明年兑现。在消费、政策、新品周期三重利好下，有望在调整后再次实现戴维斯双击。</t>
+**1. 记者（人民日报 张宇）**：大美丽法案对美股、美债和美元流动性具体有什么影响？是否会通过影响港股流动性，进而改变外围资金流向？
+**刘刚凯文**：大美丽法案三大块：提高债务上限约5万亿美元、延长2017年减税法案（新增支出3.4万亿美元，每年3400亿）、取消899条款。关税收入每年约3000-4000亿，可弥补支出，财政赤字率维持在5-6%。7-9月财政部发债约1万亿美元，可能推高美债利率，参考2023年三季度从3.8%升至5%，美股下跌4-5%。期限溢价已处于2013年以来高位，美债利率可能不会升至5%以上。对港股流动性边际偏负面，但基本面强可盖过影响。
+**2. 记者（新华社 王琳）**：关税政策目前有哪些新变化？对通胀和美联储降息路径有何影响？
+**刘刚凯文**：关税四点信息：一定会做、需维持一定税率（约10%）、不能太高、市场逐渐脱敏。新变化：时间拖后（原7月9日）、大部分国家税率相比4月2日回落，除巴西外。加拿大、墨西哥、欧盟贸易占比高，需重点谈判；其他国家对有效税率影响小，日本占比仅4.5%。有效税率当前10-12%，若8月1日全回去，可能回到10-15%，最极端18%。通胀压力缓慢抬升，年底可能升至3.3-3.4%。美联储7月降息勉强，9月后可能降息。
+**3. 记者（财新 李静）**：对中国关税目前是什么水平？中美谈判有哪些需要关注的节点？
+**刘刚凯文**：对中国关税约40-50%。需关注8月12日中美谈判及转口限制，越南转口限制40%，我们比这个税率还要低。越南和英国达成的协议都有对转口限制，这是需要密切关注的。
+**4. 记者（上海证券报 陈晨）**：港股流动性目前是什么状况？对恒指走势有何判断？
+**刘刚凯文**：港股5月后微观流动性释放，HIBOR大幅下降，金管局投放大量资金。港币汇率在7.84-7.85，金管局需收紧流动性，但可小幅收（如收90亿，放1000多亿）。三季度流动性供给不如二季度，IPO融资也形成约束。恒指在23000-24000区间震荡，上不去下不来。港股内部极致分化，结构性行情集中在AI互联网、创新药、新消费等。
+**5. 记者（证券时报 赵明）**：光伏反内卷政策目前有哪些具体措施？对行业各环节影响如何？
+**刘佳妮**：反内卷政策升级：2024年5月17日光伏行业协会座谈会，2025年2月国常会，6月29日人民日报发声，7月1日中财委会议，7月3日工信部座谈会。硅料环节整合最迫切：集中度高、成本曲线陡峭、供需比超200%；颗粒硅现金成本28元/公斤，尾部厂商45元/公斤。电池环节供需最好：PERC退出，TOPCon占90%，BC渗透率5-6%。光伏玻璃第二轮产能出清，7月降产30%，需出清约2万吨。多晶硅期货价格反弹至40元/公斤，现货价格上周大幅上涨（前一周35元）。硅片报价涨10%，电池涨2分钱，组件涨幅靠后约10%。
+**6. 记者（中国证券报 刘洋）**：人形机器人板块三季度有哪些催化剂？投资主线是什么？
+**郭文秀**：三季度三大主线：华为云生态、本土企业技术闭环、特斯拉硬件替代窗口。6月底华为发布CloudRobot具身智能平台，盘古世界模型支持点云和视频双模态生成。华为明确不造机器人，以RTC方式开放，探索AI agent或license收费。智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿，下半年有望加速上市。智元、宇树中标中国移动近1.2亿人形机器人采购订单。特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案。
+**7. 记者（第一财经 周婷）**：游戏板块近期调整后，估值水平如何？后续投资机会怎么看？
+**张雪琴**：游戏板块上涨接近两三个月，上周末开始调整，观点仍看好。版号发放常态化：今年6月单月发放158个（国产147个，进口11个），2018年以来单月最高。今年1-5月游戏市场规模同比增长17%，手游同比增长20%。估值：TTM PE约30倍，2023年AI行情到过45倍；2025年静态PE约20倍。游戏行业逆周期性，政策支持，新品周期延续，利润滞后到明年兑现。建议关注新品市场表现、用户获取下载榜排名等领先指标。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>109.9</v>
+        <v>102.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22868/10550</t>
+          <t>22868/9371</t>
         </is>
       </c>
     </row>
@@ -3825,77 +3793,56 @@
       <c r="C10" t="inlineStr">
         <is>
           <t># 课程概况
-本节班会以“梦想”为主题，由老师（发言者2）主持，面向全班同学开展。课程通过提问引入、教师个人经历分享、视频观摩、小组讨论和梦想清单书写等环节，引导学生认识梦想、思考实现梦想的条件，并鼓励学生制定和坚持自己的梦想。
-老师分享了自己成为受学生喜爱的优秀人民教师的梦想，以及曾梦想考中国美术学院（单考已过但因离家远、没钱未去）、后就读广东技术师范大学（原民族学院）并定向回龙川县教书的经历，还讲述了大学期间加入学生会、参加比赛、保持专业排名第一（专业41人）、考取教师资格证等梦想清单。班会播放了航模爱好者何宗发和普通歌手追梦的视频，老师引导学生讨论实现梦想的条件，学生提出坚持、努力、勇敢、机会、兴趣、能力、学习等，老师强调学习、坚持、行动是必不可少的三个条件，并指出梦想可以分阶段实现，要量力而行并适时调整。班会最后，老师要求每个小组的第1个同学收齐组员的梦想，并决定在班会课结束时，以自愿为原则，请想当歌手的同学上来唱一首。
+本节主题班会围绕“梦想”展开，老师通过分享个人梦想与经历、播放追梦视频、组织讨论与书写梦想清单等方式，引导学生认识梦想、思考实现梦想的条件，并鼓励学生制定自己的梦想清单。班会内容共5个大点，包括丑小鸭的梦想、老师的梦想、梦想观察团游戏、马云案例及梦想清单书写。同学们分享的梦想包括当保安、喜剧人、太空人、世界冠军、歌手等；老师的梦想是成为受学生喜爱的有名望的优秀人民教师，并讲述了自己曾经的梦想清单：考中国美术学院（单考通过但未去上）、加入学生会、参加比赛、保持专业排名第一（专业41人）、考取教师资格证等。老师高中时立志考中国美术学院，因离家远和家庭经济原因选择定向师范（免学费，毕业后回龙川县教书），当时哭了三天，但后来逐渐喜爱教师行业。老师播放视频展示航模爱好者何宗发（中国唯一去法国巴黎比赛，目标是参加明年世界锦标赛，表演飞机有真实原型机歼10）和想成为歌手的普通人（通过后天学习和努力改善唱歌走调）的追梦故事，同学们讨论实现梦想的条件，提到坚持、努力、勇敢、机会等，老师总结学习、坚持、行动是必不可少的三个条件。老师以马云为例（中考考两次、高考考多次，最终成为中国首富，新梦想是未来15年世界因他们而改变），说明梦想可以逐步调整，如先考进年级前百，再考进前50。老师分享自己的梦想之路：考上大学用了11年，获得优秀班干部用了2年，获得国家励志奖学金用了1年，成为优秀人民教师时间待定。老师让同学们写下自己的梦想清单，包括梦想、实现时间、收获等，并分享了一些同学的梦想：考试不犯糊涂、考上重本、211、成为设计师、大学四年攒20万、考630分、成为人民教师等。老师总结梦想要量力而行，可以调整，通过努力和坚持去实现。
 # 核心知识点梳理
 ## 梦想的定义与价值
-- **梦想的普遍性**：老师以提问开场，学生纷纷分享梦想——当保安、当喜剧人、当太空人、当世界冠军、当歌手等，老师指出「每个班都有想当太空人的」，说明广告词深入人心。
-- **梦想值得尊重**：老师强调「每一个梦想都是值得我们尊重的」，即使唱歌走调的人通过后天学习也可以调整过来，**不要去嘲笑任何一个人的梦想**。
-- **梦想与目标分层**：梦想可以一步步立高，如航模小伙从想在中国比赛到想走向全世界；学生可先定考进年级前百，再调整目标为前50，**分阶段实现梦想**。
-- **梦想的独特性**：针对「马云梦想不可复制」的观点，老师指出**每个人的梦想都是独一无二、不可复制的**。
+- **梦想的多样性**：同学们分享的梦想包括当保安、当喜剧人、当太空人、当世界冠军、当歌手等，老师指出每个班都有人想当太空人，说明广告词深入人心。
+- **梦想值得尊重**：老师强调“**不被嘲笑的梦想不是好梦想**”，每一个梦想都值得我们尊重，不要去嘲笑任何一个人的梦想。
+- **梦想的可调整性**：梦想可以一步步立高，如先定考进年级前百的小目标，实现后再调整为前50；也可以制定多个梦想，先定小目标再定大目标，实现几率更大。
+## 老师的梦想之路
+- **当前梦想**：老师的梦想是成为**受学生喜爱的有名望的优秀人民教师**，目前仍在努力过程中，尚未实现。
+- **曾经的梦想清单**：包括考中国美术学院（单考已通过但未去上）、加入学生会并举办新生晚会、参加各种比赛（如校运会）、保持专业排名第一（专业共41人）、考取教师资格证。
+- **定向师范的选择**：因离家远和家庭经济原因选择定向师范，免学费但毕业后须回龙川县教书；当时哭了三天，后逐渐喜爱教师行业；定向生不能在校考研，只能在职考研且学费自理。
+- **梦想之路时间线**：从读书到考上大学用了**11年**，获得优秀班干部用了**2年**，获得国家励志奖学金用了**1年**，成为优秀人民教师的时间**待定**。
 ## 实现梦想的条件
-- **坚持与努力**：老师强调「学习、坚持、行动是梦想条件必不可少的三个」，并以自己大学4年保持专业排名第一为例，说明需要每天5点起床的自律与坚持。
-- **勇敢与行动**：老师表扬班里一位同学虽然被起哄，仍勇敢站上讲台唱歌，鼓励同学们要有勇气去行动。
-- **机会与准备**：老师指出「机会永远都是留给有准备的人」，实现梦想还需要兴趣、能力与学习等条件。
-- **天赋与后天**：老师以唱歌为例，指出有人天生天籁之音，有人唱歌走调，但**走调可以通过后天学习和努力调整过来**，天赋只是1%，后天努力更重要。
-- **条件缺失的影响**：老师引导学生讨论「缺少一个条件梦想还会不会实现」，小结为具备条件越多，梦想实现越快；缺少某些条件，梦想仍有可能实现。
-## 老师的个人梦想之路
-- **当前梦想**：老师梦想成为**受学生喜爱的有名望的优秀人民教师**，目前仍在努力过程中，学生表示「在我们心目中已经成为」。
-- **高中梦想**：老师高中时梦想考**中国美术学院**，曾在国旗下讲话当着全校面宣布，被底下很多人嘲笑，但单考已通过。
-- **未去美院的原因**：老师未去中国美术学院，一是因为**离家太远**，二是因为**没钱**——学美术很费钱，老师高中靠大家资助一路成长。
-- **大学经历**：老师就读**广东技术师范大学**（原民族学院，后改名广师大），通过定向生政策（本科6年、免学费）定向回龙川县教书，当时因不情愿**哭了三天**，现在很感谢父母的选择。
-- **大学梦想清单**：老师大学期间梦想包括加入学生会、参加各种比赛（如校运会）、保持专业排名第一（专业共41人）、考取教师资格证等。
-- **定向生限制**：定向生**不能在校考研**，但可以**在职考研**——边工作边读研，且学费需自己交。
-- **梦想之路时间线**：从读书到考大学经历**11年**；录取优秀班干部用了**2年**（学校实行班团一体化，班长兼团支书）；获得国家励志奖学金用了**1年**；成为优秀人民教师的时间**待定**。
-## 视频案例：航模爱好者与歌手
-- **航模小伙何宗发**：视频中人物，**中国唯一去法国巴黎比赛的航模选手**，目标是带着飞机环游世界、把中国国旗挂在世界各大赛场。
-- **何宗发的表演**：其表演的飞机有真实原型机**歼10**，每次表演都展现技术突破，被评价「不断挑战自己极限」，并计划在**明年世界锦标赛**再比高下。
-- **何宗发的成长**：从想在中国比赛到想走向全世界，梦想一步步立高；去中国航空博物馆后，要在模型上运用同样的原理。
-- **普通歌手案例**：视频中普通人在宿舍练歌，有人天生天籁之音，有人唱歌走调被嘲笑，但**通过后天学习可以调整**，仍有可能成为歌手。
-- **视频的教育意义**：老师总结视频内容——航模小伙通过一步步努力走上更大舞台，让世界冠军看到他的成长，航模事业做得**风生水起**。
+- **核心三条件**：老师总结**学习、坚持、行动**是实现梦想必不可少的三个条件；机会永远留给有准备的人。
+- **其他条件**：包括勇敢（如同学勇敢站上讲台唱歌）、兴趣、能力、努力等；天赋只是1%，后天努力可以弥补不足。
+- **视频案例**：航模爱好者何宗发是中国唯一去法国巴黎比赛的选手，目标是参加明年世界锦标赛，表演飞机有真实原型机歼10；普通人想当歌手，通过后天学习和努力可以改善唱歌走调。
+- **马云案例**：中考考了两次才考上高中，高考考了多次，最终成为中国首富；新梦想是未来15年世界因他们而改变，享受改变他人的乐趣。
 ## 梦想清单的制定
-- **梦想清单方法**：老师示范梦想清单写法——列出第1个、第2个、第3个梦想，实现后打勾，并思考实现梦想需要的时间及实现后的收获。
-- **学生梦想示例**：老师分享学生写的梦想，如考试不犯糊涂、考上重本或211、成为医学专业学生、多一些勇气、大学4年攒20万、成为设计师、考到630分、成为人民教师等。
-- **梦想的实在性**：老师提醒学生写梦想要「实在一点、诚恳一点」，如一位学生写「希望父母身体健康」「娶一个贤惠的妻子」，老师评价「非常不错」。
-- **梦想数量与实现几率**：老师指出梦想可以制定多个，也可以只写一个；**梦想清单列得多，实现几率相对较大**，可先定小目标再定大目标。
-- **梦想的调整**：老师强调梦想需要**量力而行**，实现不了可以调整目标去实现它，通过努力坚持去实现。
+- **书写要求**：老师要求同学们拿出纸写下自己的梦想清单，包括梦想内容、实现所需时间、实现后的收获，实现后可打勾。
+- **学生梦想示例**：包括考试不犯糊涂、考上重本或211、成为设计师、大学四年攒20万、考630分、成为人民教师、父母身体健康、世界和平等。
+- **梦想调整原则**：梦想要量力而行，实现不了可以调整目标；追梦的人特别充实，梦想或许坚持到底，也许会受挫折。
 # 课堂互动与答疑
-**学生**：老师，您当初单考过了中国美术学院，为什么最后没去读？
-**教师**：两个原因：一是离家太远，二是学美术费用高，我高中是靠大家资助读完的。后来父母选了能定向回龙川县教书的学校，我就去了广东技术师范大学（原民族学院），定向生免学费，但本科六年不能考研，只能在职考研，学费自付。
-**学生**：老师，您大学四年专业排名第一，是怎么做到的？
-**教师**：每天坚持5点起床，大学四年保持本专业41人中排名第一。自律和坚持是关键，不是靠天赋，而是靠日复一日的行动。
-**学生**：老师，您说定向生不能考研，那以后想提升学历怎么办？
-**教师**：定向生不能在校读研，但可以边工作边读研，学费自己交。我现在工作后就可以走这条路，这是定向生唯一的考研方式。
-**学生**：老师，您高中在国旗下讲话说要考中国美术学院，当时被嘲笑了，您怎么看？
-**教师**：不被嘲笑的梦想不是梦想。当时我当着全校的面说一定要考上，虽然很多人嘲笑，但我单考确实过了。所以有了梦想就要努力去实现，每一个梦想都值得尊重。
-**学生**：老师，实现梦想需要哪些条件？
-**教师**：坚持、努力、勇敢、机会、兴趣、能力、学习都是条件，其中学习、坚持、行动是必不可少的三个。机会永远留给有准备的人，天赋只占1%，后天努力更重要。
-**学生**：老师，如果梦想实现不了怎么办？
-**教师**：可以分阶段调整目标。比如想考年级前50，考不进就先定前100，考进后再往前50努力。梦想可以一步步立高，像航模小伙何宗发，一开始想在中国比赛，后来想走向全世界。
-**学生**：老师，唱歌走调的人能成为歌手吗？
-**教师**：可以。视频里那个普通人在宿舍练歌，虽然天生嗓子走调，但通过后天学习和努力可以调整过来。所以不要嘲笑任何人的梦想，尽管他现在唱得不好，顶峰相见。
+**学生**：实现梦想需要具备哪些条件？缺少一个条件梦想还能实现吗？
+**教师**：实现梦想需要坚持、努力、勇敢、机会、兴趣、能力和学习等条件。缺少某一个条件，梦想仍有可能实现；但条件都具备时，梦想会实现得更快。学习、坚持、行动是必不可少的三个条件，机会永远留给有准备的人。
+**学生**：如果考不进年级前50，梦想实现不了怎么办？
+**教师**：梦想可以量力而行、逐步调整。考不进前50就先调整为考进前百，考进前百后再定前50的目标，一步步往前进。梦想不必一次定得过高，先定小目标再定大目标，实现几率更大。
+**学生**：定向师范生可以考研吗？
+**教师**：定向生不能在校全日制考研，但可以在职考研——边工作边读研，学费需自己承担。老师当年选择定向师范是因为离家远、家庭经济条件有限，定向免学费，毕业后回龙川县教书。
 # 课后任务与学习建议
 ## 课堂练习
-- **梦想条件讨论**：以4个大组为观察团，观察航模爱好者何宗发与想当歌手的普通人两个追梦案例，找出实现梦想所需条件，学生提出坚持、努力、勇敢、机会、兴趣、能力、学习等。
-- **梦想清单书写**：学生拿出纸写下自己的梦想清单，可参照老师示范列多条梦想，每条注明实现所需时间与预期收获，写完后由每组第1个同学收齐交给老师。
+- **梦想观察团游戏**：全班分4个大组，每组为一个观察团，观察对象是玩航模的小伙子和想成为歌手的普通人，讨论实现梦想需要具备哪些条件。
+- **梦想清单书写**：每人拿出纸写下自己的梦想清单，列出第1个、第2个、第3个梦想，并注明实现所需时间及实现后的收获；写完后由每个小组第1个同学收齐交给老师。
+- **梦想分享点评**：老师展示并点评部分同学的梦想清单，如考试不犯糊涂、考上重本或211、成为设计师、大学四年攒20万、考630分、成为人民教师等，肯定朴实可行的梦想。
 ## 复习重点
-- **实现梦想的三大必备条件**：学习、坚持、行动，三者缺一不可，同时具备则梦想实现更快。
-- **梦想需分阶段调整**：目标实现不了时可先调整为更易达成的阶段性目标（如先考进年级前百再冲前50），量力而行、逐步提高。
-- **梦想值得尊重**：不被嘲笑的梦想不是梦想，不要嘲笑任何人的梦想，每个梦想都是独一无二、不可复制的。
-- **机会留给有准备的人**：实现梦想需要机会，但机会永远留给有准备的人，需以兴趣、能力与学习作支撑。
+- **梦想的定义与价值**：每个梦想都值得尊重，不被嘲笑的梦想不是好梦想；梦想可以有多个，先定小目标再定大目标，实现几率更大。
+- **实现梦想的条件**：学习、坚持、行动是必不可少的三个条件；此外还需勇敢、机会、兴趣与能力，机会永远留给有准备的人。
+- **梦想的调整原则**：目标实现不了时可以量力而行地调整，如先考进年级前百再考进前50，一步步往前推进；追梦路上可能受挫折，但追梦的人是充实的。
+- **梦想的逐步升级**：梦想实现后可立得更高，如航模爱好者何宗发从国内走向世界锦标赛；老师以马云为例说明起点高低不重要，关键在坚持。
 ## 学习建议
-- **制定梦想清单**：参照老师示范，用漂亮纸张列出梦想清单，逐条写明实现所需时间与收获，实现后打勾，可同时制定多个梦想以增加实现几率。
-- **分阶段设定目标**：先定小目标再定大目标，如考不进年级前50就先调整为前百，考进后再冲前50，一步步向前推进。
-- **勇敢行动与坚持**：像班内同学勇敢站上讲台唱歌一样，敢于行动；老师大学4年保持专业排名第一（专业41人），靠的是每天5点起床的自律与坚持。
-- **结合现实调整梦想**：老师曾梦想考中国美术学院（单考已过），因离家远、没钱最终选择定向师范，提醒学生梦想需结合家庭条件与现实情况量力而行。</t>
+- **制定梦想清单**：参照老师示范，按时间顺序列出多个梦想（如考上大学用了11年、获优秀班干部用了2年、获国家励志奖学金用了1年），实现后打勾并记录收获。
+- **分步设定目标**：将大梦想拆解为可逐步达成的小目标，如先考进年级前百再冲刺前50；梦想写实在一点、诚恳一点，避免空泛。
+- **勇敢行动与坚持**：像班里同学勇敢站上讲台唱歌一样，有梦想就要付诸行动；老师提醒坚持每天5点起床保持专业排名第一（专业41人），自律与坚持是关键。
+- **不嘲笑他人梦想**：老师强调不要嘲笑任何人的梦想，唱歌走调可通过后天学习和努力调整过来；对同学的梦想要相信并给予支持。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>57.7</v>
+        <v>49.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9362/3836</t>
+          <t>9362/2984</t>
         </is>
       </c>
     </row>
@@ -4070,103 +4017,96 @@
       <c r="C11" t="inlineStr">
         <is>
           <t># 全文摘要
-本期新闻联播围绕国内发展成就与国际动态展开，涵盖文化自信与改革、赵乐际访俄、夏粮丰收、铁路货运、快递业、油气管网建设、防汛应对、国内联播快讯及国际新闻等板块。习近平总书记提出“两个结合”，强调文化自信对民族复兴的意义；2023年6月召开文化传承发展座谈会，10月首次提出习近平文化思想，并审议通过《深化文化体制改革实施方案》等文件，我国已成为图书、电视剧、动漫等领域生产大国。赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议；今年是中俄建交75周年，沃洛金表示俄坚定恪守一个中国原则。
-今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤。全国已建成高标准农田10亿多亩，中央财政首次提前下拨16亿元小麦“一喷三防”资金。6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%；中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。上半年我国快递业务量超800亿件，快递企业已运行国际航线40余条。我国油气管网加速建设，预计全年新增管道里程超4000公里，主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%。重庆28个区县出现暴雨，其中13个区县大暴雨；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程。国内快讯方面，北京上半年320个市区重大项目全部开工，总投资超过4000亿元；燕矶长江大桥北岸主塔封顶，主跨1860米；第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员参赛。国际方面，特朗普在竞选集会遭未遂刺杀，右耳中枪受伤，一名观众死亡；以军空袭加沙地带马瓦西地区致90人死亡，约300人受伤；加拿大东北部林火蔓延，过火面积100平方公里，9600人被疏散。
+本期新闻联播围绕国内发展成就与国际动态展开，涵盖文化自信与改革、赵乐际访俄、夏粮丰收、铁路货运、快递业、油气管网、防汛、国内联播快讯及国际新闻等板块，主线为展示中国改革发展成就与国际形势。文化体制改革方面，习近平总书记提出把中华优秀传统文化精华与马克思主义立场观点方法结合，2023年10月首次提出习近平文化思想；赵乐际于7月9日至13日对俄罗斯进行正式友好访问，会见普京并出席中俄议会合作委员会第九次会议。国内经济数据方面发布了夏粮、货运、快递等多组创新高数据，其中夏粮产量达2996亿斤创历史新高，6月国家铁路发送货物3.32亿吨，上半年快递业务量超800亿件。国际方面，特朗普在竞选集会遭未遂刺杀，以军空袭加沙马瓦西地区致90人死亡。本期以播报国内外重要新闻为主，未形成明确结论。
 # 分段速览
 ## 00:00-08:31 文化自信与改革
-习近平总书记以重大理论创新指导文化体制改革实践，在“五位一体”总体布局中对文化建设作出战略部署。总书记在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时，强调要善于从中华优秀传统文化中汲取治国理政理念，以时代精神激活其生命力。2023年6月主持召开文化传承发展座谈会，系统论述中华文明五个突出特性；同年10月全国宣传思想文化工作会议首次提出习近平文化思想。
-中央审议通过《深化文化体制改革实施方案》和《关于实施中华优秀传统文化传承发展工程的意见》，推动文化领域供给侧结构性改革，文化旅游深度融合、非遗保护制度日益完善，我国成为图书、电视剧、动漫等领域生产大国。
-## 08:39-12:31 赵乐际访俄
-全国人大常委会委员长赵乐际应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。赵乐际在圣彼得堡会见总统普京，转达习近平主席的亲切问候，表示今年是中俄建交75周年，愿从立法机构层面落实两国元首重要共识。在莫斯科与马特维延科、沃洛金分别会谈时，强调要在涉及彼此核心利益问题上坚定相互支持，深化多层级、多领域、多渠道交流合作。10日出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、以法治方式促进务实合作等五点建议。访问期间向俄无名烈士墓敬献花圈。
-## 12:49-13:57 夏粮产量创历史新高
+新闻开篇综述党的十八大以来文化体制改革成就。习近平总书记以重大理论创新指导实践，在“五位一体”总体布局中对文化建设作出战略部署，引领文化强国建设取得历史性成就。总书记在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时，强调要善于从中华优秀传统文化中汲取治国理政理念，并以时代精神激活其生命力。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。文化领域供给侧结构性改革深入推进，文旅融合、非遗保护、公共文化服务体系等不断完善，我国成为图书、电视剧、动漫等领域生产大国。
+## 08:31-12:39 赵乐际访俄
+全国人大常委会委员长赵乐际应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。赵乐际在圣彼得堡会见总统普京，转达习近平主席的亲切问候，表示今年是中俄建交75周年，两国立法机构应落实元首共识、巩固政治互信。普京请赵乐际转达对习近平的问候，强调俄中立法机构高水平合作有助于推进双边合作优先议题。赵乐际与马特维延科、沃洛金分别会谈，就核心利益相互支持、深化多层级交流合作等达成共识。
+10日，赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验等五点建议，并在莫斯科向无名烈士墓敬献花圈。
+## 12:39-14:21 夏粮丰收
 今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，夏粮首战告捷为全年粮食丰收奠定坚实基础。
-## 14:28-15:43 6月份国家铁路货运指标
-6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高，我国铁路货运量、货运周转量等指标稳居世界首位。分品类看，化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高。多式联运快车已覆盖各省会城市，铁海快线班列覆盖全国主要港口。中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%，有力保障国际供应链产业链稳定畅通。
-## 16:10-17:07 上半年快递业发展
-今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件。快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，国际运输能力稳步增强。多地启用、升级跨境仓，农村寄递网络覆盖范围逐渐扩大，每天超1亿多件快递包裹在农村地区流动。5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。快递业不断丰富服务场景，实现与制造业的融合发展。
-## 17:29-18:41 油气管网建设
-今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。到2025年将初步形成东北、西北、西南及海上四大油气战略通道，建成“五纵五横”天然气干线管网。
-## 19:20-20:40 防汛与降雨应对
-重庆28个区县出现暴雨，其中13个区县大暴雨，当地连夜抢险排涝保障道路畅通；四川暴雨造成内江部分地区内涝、滑坡，消防救援人员转移被困群众；安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，处置堤防渗漏和管涌。水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
-## 20:41-23:38 国内联播快讯
-北京上半年320个市区重大项目全部开工，总投资超过4000亿元，聚焦现代化产业、基础设施、城市更新等领域。燕矶长江大桥北岸主塔封顶，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军。内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底。“中非儿童手拉手”活动在中国儿童中心启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表参加。
-## 23:47-24:29 国际反响与特朗普遇刺
-多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量。13日在美国宾夕法尼亚州巴特勒市举行的特朗普竞选集会发生枪击，特朗普右耳中枪受伤，一名观众死亡、两名观众受重伤。枪手从集会现场外高处向演讲台开枪，所处屋顶距离演讲台约180多米到270多米，开枪后被特勤局狙击手打死。美联邦调查局称特朗普遭未遂刺杀，枪手为20岁左右男性，来自宾夕法尼亚州，作案动机待查明。
-## 26:00-28:37 中东局势
-以军13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤。以色列总理内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马。巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等也发表声明予以谴责。以军还在拉法、加沙城等地打击巴武装人员，巴武装派别使用迫击炮、火箭弹打击以军目标。黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，黎真主党武装打击了以色列北部的以军集结地和情报设施。叙利亚首都大马士革多个地点遭空袭，造成1名政府军士兵死亡、3人受伤。
-## 28:42-29:24 俄乌冲突与加拿大林火
-俄罗斯国防部称使用“伊斯坎德尔-M”导弹打击了哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备。乌克兰武装部队总参谋部称乌军在前线地区与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。加拿大东北部纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散，消防人员称已无法继续使用灭火飞机。加拿大目前正应对500多起活跃林火，其中超400起处于失控状态。
-## 30:14-30:27 全面深化改革专题
-本期《全面深化改革中国式现代化万千气象》专题聚焦上海、浙江两地，展示其在新时代新征程上坚定不移全面深化改革、扩大开放，在推进中国式现代化建设中走在前列的实践。
+## 14:21-16:03 铁路货运
+6月份国家铁路货运多项指标创历史同期新高。国铁集团数据显示，6月国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，铁路货运量、货运周转量稳居世界首位。分品类看，化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。多式联运快车已覆盖各省会城市，铁海快线班列覆盖全国主要港口。国际联运方面，6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
+## 16:03-17:22 快递业
+今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件，行业发展提速。快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，国际运输能力稳步增强。多地启用、升级跨境仓，农村寄递网络覆盖范围逐渐扩大，每天超1亿多件快递包裹在农村地区流动。5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。快递业不断丰富服务场景，实现与制造业的融合发展。
+## 17:22-19:12 油气管网
+今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里，“全国一张网”不断完善。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。到2025年将初步形成四大油气战略通道，建成“五纵五横”天然气干线管网。
+## 19:12-20:40 防汛应对
+重庆九龙坡、江北等28个区县出现暴雨，其中13个区县大暴雨，当地组织人员连夜抢险排涝。四川内江出现内涝、滑坡等险情，消防救援人员转移被困群众。安徽滁州全椒县工作人员加强巡堤，处置堤防渗漏和管涌。水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+## 20:40-23:38 国内联播快讯
+北京上半年计划新开工的320个市区重大项目已全部开工，总投资超4000亿元，聚焦现代化产业、基础设施、城市更新等领域。燕矶长江大桥北岸主塔封顶，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运重要过江通道。第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军。内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底。外交部、全国妇联主办的“中非儿童手拉手”活动在京启动，五国儿童代表将在北京、河南参观访问。
+## 23:38-28:37 国际新闻
+多国人士高度关注即将召开的党的二十届三中全会，表示中国全面深化改革、扩大开放为世界提供更广阔市场和发展机遇。美国前总统特朗普在宾夕法尼亚州竞选集会遭未遂刺杀，右耳中枪，一名观众死亡、两名重伤，枪手被特勤局狙击手打死。以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法。以军袭击黎巴嫩多个边境村镇，真主党武装打击以军集结地。叙利亚大马士革遭空袭，造成1名政府军士兵死亡、3人受伤。
+## 28:37-30:27 国际联播快讯
+俄罗斯国防部称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁20件乌军装备；乌克兰武装部队总参谋部称击退俄军17次进攻。加拿大东北部纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散，加拿大正应对500多起活跃林火，其中超400起失控。节目最后预告《全面深化改革中国式现代化万千气象》专题，走进上海、浙江，展示两地全面深化改革、扩大开放的实践。
 # 要点梳理
 ## 文化自信与改革
-- **理论创新**：习近平总书记提出“两个结合”，即把马克思主义基本原理同中国具体实际、同中华优秀传统文化相结合，为坚持和发展马克思主义文化理论作出重大原创性贡献。
-- **实地调研**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院凝望“实事求是”匾额，指出一定要把真理本土化；在三苏祠强调汲取治国理政理念；在武夷山朱熹园提出以时代精神激活中华优秀传统文化生命力。
-- **习近平原话**：“我们五千年的文明，我们要尊重，也要弘扬，把它里边精华的东西和我们现在所坚持的马克思主义立场、观点、方法结合起来，这就是中国特色社会主义。”
+- **习近平总书记论述**：提出把中华优秀传统文化精华与马克思主义立场观点方法结合，强调“我们五千年的文明，我们要尊重，也要弘扬”。
+- **考察足迹**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院凝望“实事求是”匾额，指出一定要把真理本土化；在三苏祠强调汲取治国理政理念和思维；在武夷山朱熹园提出以时代精神激活传统文化生命力。
 - **文化传承发展座谈会**：2023年6月，习近平总书记主持召开，系统论述中华文明五个突出特性，阐述“两个结合”尤其是“第二个结合”的重大意义。
-- **习近平文化思想**：2023年10月全国宣传思想文化工作会议首次提出，引领新征程文化改革发展工作打开新局面。
-- **改革方案**：《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署。
-- **文化事业成果**：深入实施中华文明探源工程，高标准推进国家文化公园建设，中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版。
+- **习近平文化思想**：2023年10月全国宣传思想文化工作会议首次提出，引领新征程文化改革发展打开新局面。
+- **《深化文化体制改革实施方案》**：中央全面深化改革领导小组审议通过的第一个专项小组改革方案，为文化改革发展谋篇布局。
+- **《关于实施中华优秀传统文化传承发展工程的意见》**：首次以中央文件形式对文化传承发展进行部署，推动创造性转化、创新性发展。
+- **文化领域成就**：文化旅游深度融合、非遗保护传承制度日益完善、公共文化服务体系不断健全；深入实施中华文明探源工程，高标准推进国家文化公园建设；中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版。
 - **文化产业数据**：我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
 ## 赵乐际访俄
-- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议。
-- **中俄关系定位**：今年是中俄建交75周年，在两国元首战略引领下，中俄新时代全面战略协作伙伴关系高水平、高质量发展。
-- **赵乐际表态**：中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献。
-- **普京表态**：俄中立法机构始终保持高水平合作，加强俄中议会合作委员会工作有利于两国交流经验、互学互鉴，促进立法、地方等各领域合作。
-- **会谈共识**：以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持；用好中俄议会合作委员会、双边友好小组等机制和平台，互学互鉴立法经验。
+- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问。
+- **会见普京**：在圣彼得堡会见总统普京，转达习近平主席亲切问候；赵乐际表示今年是中俄建交75周年，两国新时代全面战略协作伙伴关系高水平、高质量发展。
+- **普京表态**：请赵乐际转达对习近平主席的亲切问候，称俄中立法机构保持高水平合作，加强议会合作委员会工作有利于两国交流经验、互学互鉴。
+- **与马特维延科、沃洛金会谈**：赵乐际表示要以两国元首重要共识为指引，在涉及彼此核心利益问题上坚定相互支持；两国立法机构要深化多层级、多领域、多渠道交流合作。
 - **马特维延科表态**：发展对华关系得到俄社会广泛认同和支持，两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流。
 - **沃洛金表态**：俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
-- **议会合作委员会致辞**：赵乐际指出两国立法机构要密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作，从立法机构层面团结壮大“全球南方”力量。
-- **其他行程**：访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
+- **中俄议会合作委员会第九次会议**：7月10日赵乐际出席并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作五点建议。
+- **敬献花圈**：访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
 ## 夏粮产量
-- **总产量**：今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，克服多重自然灾害影响。
-- **单产数据**：夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加主要原因。
-- **支撑措施**：全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金。
-- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，夏粮首战告捷为全年粮食丰收奠定坚实基础。
-## 6月铁路货运
-- **总体指标**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
-- **分品类数据**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高。
-- **境内网络**：多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口。
+- **总产量**：今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。
+- **单产数据**：夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤；单产恢复性增长是产量增加的主要原因。
+- **增产措施**：全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金。
+- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，得益于集成技术推广、科学防灾减灾、收割晾晒及时。
+## 铁路货运
+- **总体数据**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；铁路货运量、货运周转量稳居世界首位。
+- **重点物资**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高。
+- **境内网络**：连接内陆物流节点城市的多式联运快车覆盖各省会城市，铁海快线班列覆盖全国主要港口。
 - **国际联运**：6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
-## 上半年快递业
-- **业务总量**：截至6月30日，今年我国快递业务量已达800亿件，行业发展提速。
-- **国际运输**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，多地启用、升级跨境仓。
-- **农村网络**：每天超1亿多件快递包裹在农村地区流动，5—6月生鲜商品进入销售旺季，快递日均业务量近5亿件。
+## 快递业
+- **业务总量**：上半年快递业务量超800亿件，截至6月30日已达800亿件。
+- **国际运输**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线。
+- **农村网络**：每天超1亿多件快递包裹在农村地区流动；5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。
 - **融合发展**：快递业不断丰富服务场景，实现与制造业的融合发展。
-## 油气管网建设
-- **年度目标**：预计全年新增管道里程超4000公里，“全国一张网”不断完善。
-- **重点工程**：西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
-- **管网现状**：主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。
-- **2025年规划**：初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”的天然气干线管网。
-## 防汛与降雨应对
-- **重庆汛情**：7月13日8时至14日8时，重庆28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝。
-- **四川汛情**：暴雨造成内江部分地区内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。
-- **安徽汛情**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，处置堤防渗漏和管涌。
-- **水利部部署**：针对“七下八上”防汛关键期逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程；联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+## 油气管网
+- **建设目标**：预计全年新增管道里程超4000公里，“全国一张网”不断完善。
+- **西气东输四线**：已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
+- **管网能力**：主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%；天然气“全国一张网”日供气能力超10亿立方米。
+- **2025年规划**：初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网。
+## 防汛
+- **重庆雨情**：7月13日8时至14日8时，28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨；当地组织工作人员连夜抢险排涝。
+- **四川险情**：暴雨造成内江部分地区内涝、滑坡，消防救援人员紧急出动转移被困群众。
+- **安徽汛情**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌。
+- **水利部部署**：针对“七下八上”防汛关键期逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程。
+- **联合调度**：水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
 ## 国内联播快讯
-- **北京重大项目**：上半年计划新开工的320个市区重大项目全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超过4000亿元。
-- **燕矶长江大桥**：7月14日北岸主塔封顶，下一步转入主缆施工阶段；连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系重要过江通道。
-- **环青海湖自行车赛**：第二十三届7月14日在海北州门源县收官，8天8个赛段，国内外22支车队154名运动员参赛，决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
-- **草原那达慕**：内蒙古第34届7月14日在锡林浩特市开幕，主题“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
-- **中非儿童手拉手**：由外交部、全国妇联主办，7月14日在中国儿童中心启动；来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问。
+- **北京重大项目**：上半年计划新开工的320个市区重大项目全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，总投资超4000亿元。
+- **燕矶长江大桥**：7月14日北岸主塔封顶，下一步转入主缆施工阶段；大桥连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路。
+- **环青海湖国际公路自行车赛**：第二十三届7月14日在海北州门源县收官，8天8个赛段，国内外22支车队154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
+- **草原那达慕**：内蒙古第34届7月14日在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
+- **“中非儿童手拉手”活动**：7月14日由外交部、全国妇联主办，在中国儿童中心启动；纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。
 ## 国际新闻
-- **二十届三中全会关注**：多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量。
-- **特朗普遭未遂刺杀**：7月13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击，特朗普右耳中枪受伤、竞选团队称其“状况良好”；一名观众死亡、两名观众受重伤；枪手从集会现场外高处开枪，距演讲台约180多米到270多米，被特勤局狙击手打死；美联邦调查局称枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明。
-- **以军空袭加沙**：以军13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者包括许多妇女和儿童；内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马，今后将继续发动类似袭击；哈马斯表示袭击使局势“严重升级”。
-- **巴方及国际谴责**：巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明予以谴责。
-- **加沙其他冲突**：以军13日在拉法、加沙城等地打击巴武装人员和军用设施，巴武装派别使用迫击炮、火箭弹等打击以军阵地和坦克。
-- **黎以边境冲突**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾；黎真主党武装打击了以色列北部以军集结地及情报设施。
+- **特朗普遭未遂刺杀**：7月13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击，特朗普右耳中枪受伤，一名观众死亡、两名重伤；枪手为20岁左右男性、来自宾夕法尼亚州，从集会现场外高处开枪，被特勤局狙击手打死，作案动机待查明。
+- **以军空袭加沙**：13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者包括许多妇女和儿童；内塔尼亚胡称目标是哈马斯下属“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马。
+- **各方反应**：哈马斯称袭击使局势“严重升级”；巴勒斯坦总统阿巴斯谴责以军违反国际法；约旦、卡塔尔、埃及等发表声明予以谴责。
+- **以黎冲突**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾；黎真主党武装打击了位于以色列北部的以军集结地和情报设施。
 - **叙利亚遭空袭**：7月14日凌晨大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
-- **俄乌冲突**：俄军使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌军当天在前线与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
-- **加拿大林火**：纽芬兰与拉布拉多省林火迅速蔓延，过火面积100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大正应对500多起活跃林火，其中超400起处于失控状态。</t>
+- **俄乌冲突**：俄军使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件装备；乌军称当天与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
+- **加拿大林火**：纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；加拿大正应对500多起活跃林火，其中超400起处于失控状态。</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>76.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7755/7863</t>
+          <t>7755/6460</t>
         </is>
       </c>
     </row>
@@ -4405,148 +4345,111 @@
       <c r="C12" t="inlineStr">
         <is>
           <t># 课程概况
-本课为初中物理光学复习课，主讲人系统讲解了光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用五大模块，并通过例题巩固知识点。课程从几何光学历史引入，强调光在均匀介质中沿直线传播，光速在真空中为3×10⁸米/秒（即3×10⁵千米/秒），并列举三点一线、激光准直、小孔成像、日食月食、影子形成等实例。
-主讲人详细讲解了光的反射定律（三线共面、分居两侧、反射角等于入射角），纠正垂直入射时入射角为0度的常见错误，并区分镜面反射与漫反射，指出生活中大多数反射为漫反射，如电影院银幕、黑板反光等。平面镜成像部分，强调成像是正立、等大的虚像，实验用玻璃板代替平面镜便于确定像的位置，并分析实验误差原因（玻璃板与水平面不垂直、玻璃板有厚度）。
-球面镜部分，凸面镜对光线起发散作用，凹面镜对光线起会聚作用，应用于汽车后视镜、丁字路口反光镜、手电筒、太阳灶等，并提及玻璃幕墙形成凹面会聚光线可能烧死树木或引发火灾，造成光污染。课程最后布置了相关练习题，并预告后续将讲解光的折射与透镜。
+本课为初中物理光学复习课，主讲人系统梳理几何光学核心知识，覆盖光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用五大模块，并通过例题与生活实例巩固理解。课程从光源定义（自然光源如太阳，人造光源如火把、蜡烛、煤油灯、电灯）与光线模型（带箭头的直线，非真实存在）入手，强调光在均匀介质中沿直线传播，并列举三点一线、激光准直、小孔成像、日食月食、影子形成等实例。光速方面，真空中为3×10^8米/秒（3×10^5千米/秒），空气中略慢，水中约为真空中的3/4，玻璃中约为2/3；例题计算激光从地球到月球1.25秒，距离为3.75×10^8米。
+光的反射定律部分，主讲人明确三线共面、分居两侧、反射角等于入射角，法线为辅助线（垂直镜面、不存在），垂直入射时入射角与反射角均为0度；作图步骤为先画法线，再根据反射角等于入射角画入射光线。镜面反射与漫反射均遵守反射定律，生活中大多数反射为漫反射（如黑板、电影银幕），镜面反射易造成反光问题（如玻璃隔断撞人、黑板反光）；例题涉及雨后夜晚水潭判断（迎着月光走亮处为水潭，背着月光走暗处为水潭）及光路可逆（小明能看到小刚的像，则小刚也能看到小明）。
+平面镜成像原理为光的反射定律，成像特点为正立、等大、虚像，像与物关于镜面对称；实验用玻璃板代替平面镜便于确定像的位置，刻度尺比较像与物到镜面距离，两段相同蜡烛比较大小，光屏不能接收虚像；误差原因包括玻璃板与水平面不垂直、玻璃板有厚度（两个面反射成像）。例题涉及视力表距镜3.5米、人距镜1.5米可看到5米处虚像，以及人距平面镜1米时人与像距离2米、远离时像大小不变。球面镜部分，凸面镜发散光线（用于汽车后视镜、丁字路口镜），凹面镜会聚光线（用于手电筒、汽车前大灯、太阳灶、医生额镜），并提及玻璃幕墙凹面会聚光线可能烧死树木、引发火灾（光污染）。
+课程中穿插生活化讨论，如光源历史（从木柴到电灯）、潜水体验（光线与压强限制）、视力保护（近视率与用眼习惯）等，但均服务于光学知识讲解。课堂练习覆盖直线传播、反射定律、镜面反射与漫反射、平面镜成像等题型，主讲人逐题讲解答案与原理。
 # 核心知识点梳理
 ## 光的直线传播
-- **几何光学历史**：几何光学从**2000多年前**的古希腊时期开始研究，当时哲学家已找到直线传播和反射规律；后人将折射规律变为折射定律，初中阶段仍按规律讲授。
-- **光源定义**：自身能够发光的物体；没有光源则无光线、无反射、无折射可言。
-- **光源分类**：按来源分为自然光源（如太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）；按形状分为点光源（如蜡烛）和平行光源（如太阳光）。
-- **光线概念**：用带箭头的直线代表光线，是**物理模型**，并非真实存在；画图时点光源画成点，平行光源画平行光。
-- **直线传播条件**：光在**均匀介质**中沿直线传播；大气层不均匀时会发生偏折，如太阳越出地平线、星星眨眼。
-- **三点一线实例**：步枪瞄准时眼睛、准心尖、标尺缺口三者重合，依据是光在均匀介质中沿直线传播；队列排齐、木工看尺子是否平直同理。
-- **激光准直**：利用激光沿直线传播进行准直，是现代常用技术。
-- **小孔成像**：成**倒立实像**，放大缩小不一定；像的形状与孔的形状无关，如树荫下太阳光斑是太阳缩小的像。
-- **小孔成像实验**：纸杯底部用针扎小孔，前方蒙塑料布，点燃蜡烛置于孔前，可在塑料布上看到倒立火苗像。
-- **日食形成**：太阳、月球、地球在同一直线上，**月球在中间**；1号区域为日全食，2、3号区域为日偏食，4号区域为日环食。
-- **月食形成**：太阳、地球、月球在同一直线上，**地球在中间**；月球完全进入1号区域为月全食，部分在1号区域、部分在2或3号区域为月偏食。
-- **影子形成**：光在均匀介质中沿直线传播的实例，唐朝皮影戏即利用此原理。
-- **真空光速**：`3×10^8` 米/秒，即 `3×10^5` 千米/秒，约**每秒绕地球赤道7圈半**。
-- **介质中光速**：空气中约 `2.99×10^8` 米/秒，比真空略慢；水中约为真空的 `3/4`，玻璃中约为 `2/3`。
-- **光速计算题**：激光从地球到月球用时1.25秒，按真空光速计算，距离为 `3.75×10^8` 米。
-- **闪电与雷声**：先看到闪电后听到雷声，因为**光速比声速快**；声速在15℃时约 `340` 米/秒。
+- **光源定义**：自身能够发光的物体，分为自然光源（如太阳）和人造光源（如火把、蜡烛、煤油灯、电灯）。
+- **光线模型**：用带箭头的直线表示，是**物理模型**，并非真实存在；按来源分为自然光源与人造光源，按形状分为点光源与平行光源。
+- **传播规律**：光在**均匀介质**中沿直线传播；大气层不均匀时会发生偏折，如太阳越出地平线、星星眨眼。
+- **实例**：步枪瞄准三点一线、队列排齐、木工闭眼看尺子、激光准直；小孔成像成**倒立实像**（放大缩小不一定，与孔形状无关），树荫光斑即小孔成像。
+- **日食与月食**：日食时太阳、月球、地球在同一直线且月球在中间，1号区域日全食、2/3号区域日偏食、4号区域日环食；月食时地球在中间，月球完全在地球阴影中为月全食，部分在阴影中为月偏食。
+- **影子形成**：光沿直线传播，如唐朝皮影戏。
+- **光速**：真空中为 `3×10^8` 米/秒（`3×10^5` 千米/秒），约**一秒钟绕地球赤道7圈半**；空气中略慢，水中约为真空中的 `3/4`，玻璃中约为 `2/3`。
+- **例题**：激光从地球射到月球用时1.25秒，距离为 `3.75×10^8` 米；雷电时先看到闪电后听到雷声，因为**光速比声速快**。
 ## 光的反射定律
-- **基本概念**：`AO` 为入射光线，`OB` 为反射光线，`O` 为入射点；法线 `OP` 垂直于镜面，是入射光线与反射光线夹角的角平分线。
-- **入射角与反射角**：入射光线与法线的夹角为入射角，反射光线与法线的夹角为反射角；法线是辅助线，真实不存在，画图用虚线。
-- **反射定律三句话**：反射光线、入射光线和法线在**同一平面内**（共面）；反射光线和入射光线**分居法线两侧**；**反射角等于入射角**。
-- **垂直入射易错点** ⭐：光垂直射到镜面上时，入射角和反射角均为 **0度**，不是90度。
-- **夹角换算**：反射光线与平面镜夹角40度时，入射角为 **50度**（与法线夹角）。
-- **作图步骤**：先画法线（虚线，画2–3段即可），再根据反射角等于入射角画反射光线；作图痕迹保留法线，箭头补全。
-- **作图技巧**：用尺子刻度对准法线，在反射光线上找一点，在另一侧找对称点，连接入射点即可，不必用量角器。
-- **第10题**：入射光线与镜面夹角增大时，入射角减小、反射角减小，传播速度不变，选C。
-- **第11题**：入射光线与法线夹角60度时，反射角为 **60度**。
-- **第12题**：反射光线与入射光线夹角80度时，反射角为 **40度**（角平分线）。
+- **定律内容**：反射光线、入射光线、法线在同一平面内（共面）；反射光线与入射光线分居法线两侧；**反射角等于入射角**。
+- **法线**：辅助线，垂直镜面，不存在，画虚线；引入法线是为后续折射学习作准备。
+- **易错点**：光垂直射到镜面上，入射角与反射角均为 **0度**（不是90度）；反射光线与平面镜夹角40度时，入射角为50度。
+- **作图步骤**：先画法线（虚线，留作图痕迹），再根据反射角等于入射角画入射/反射光线，最后补全箭头；可用刻度尺对称取点法画图。
+- **例题**：入射光线与镜面夹角增大时，反射角减小、传播速度不变；入射光线与法线夹角60度时反射角60度；反射光线与入射光线夹角80度时反射角40度。
 ## 镜面反射与漫反射
-- **镜面反射**：平行光射到光滑表面，反射光仍平行；人眼恰在反射光方向才能看到，否则看不到，如商场玻璃隔断易撞人。
-- **漫反射**：平行光射到凹凸不平表面，反射光射向**各个方向**；生活中大多数反射是漫反射，如黑板、电影银幕、人的皮肤。
-- **共同规律**：镜面反射和漫反射**都遵守光的反射定律**。
-- **黑板反光**：教室某些位置看黑板只见光亮、看不清粉笔字，是黑板发生**镜面反射**。
-- **电影银幕**：白色粗糙幕布使射到屏幕上的光发生**漫反射**，保证各位置观众都能看到。
-- **雨后水潭题** ⭐：迎着月光走，地面**发亮处是水潭**（镜面反射）；背着月光走，地面**暗处是水潭**。
-- **白纸与镜子实验**：手电筒垂直照镜子和白纸，斜看时镜子是黑的、白纸是亮的，因镜子发生镜面反射、白纸发生漫反射。
-- **光路可逆**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明，依据是**光路可逆**。
+- **镜面反射**：平行光射到光滑表面，反射光平行，人眼位置决定能否看到反射光；缺点如商场玻璃隔断易撞人、黑板反光看不清粉笔字。
+- **漫反射**：表面凹凸不平，反射光向各个方向，**生活中大多数反射是漫反射**（黑板、电影银幕、投影幕布、人本身）；镜面反射与漫反射**都遵守光的反射定律**。
+- **例题**：雨后夜晚，迎着月光走亮处是水潭（镜面反射），背着月光走暗处是水潭；白纸上放小镜子，垂直照射时斜看镜子是黑的、白纸是亮的。
+- **光路可逆**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明在平面镜中的像。
 ## 平面镜成像
-- **成像原理**：平面镜成像依据**光的反射定律**，反射光线反向延长线的交点即像的位置。
-- **成像特点**：成**正立、等大的虚像**；像与物连线与镜面垂直，像到镜面距离等于物到镜面距离。
-- **实验器材选择**：用**玻璃板代替平面镜**，便于移动后方蜡烛确定像的位置；刻度尺用于比较像与物到镜面的距离；两段完全相同的蜡烛用于比较像与物的大小。
-- **虚像验证**：光屏（白塑料片、白墙等）不能接收到烛焰的像，因为实际光线未到达镜后；手放后方蜡烛处不会被烫伤。
-- **像的大小**：物体靠近玻璃板时，像的大小**不变**。
-- **实验误差原因一**：蜡烛到玻璃板距离与像到玻璃板距离不相等，可能是**玻璃板与水平面不垂直**（或与事先画好的镜面位置未重合）。
-- **实验误差原因二**：同一侧看到两个像，原因是**玻璃板有厚度**，两个面都发生反射成像；应选薄玻璃板（如3毫米）。
-- **第18题**：人在河边看到岸边树在水中的倒影属于光的反射，平静水面充当平面镜；看到河水深度比实际浅是光的折射。
-- **第21题**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子 **1.5米** 即可看到5米处的虚像。
-- **第22题**：视力表距镜子3米时，人距镜子 **2米** 即可，选B。
-- **第23题**：人站在平面镜前1米处，人与像之间的距离为 **2米**。
-- **第24题**：人向远离平面镜方向移动，镜中像的大小**不变**，选C。
+- **成像原理**：光的反射定律，像与物关于镜面对称；成**正立、等大、虚像**（与小孔成像的倒立实像不同）。
+- **实验要点**：用玻璃板代替平面镜便于确定像的位置；刻度尺用于比较像与物到镜面距离；两段完全相同的蜡烛用于比较像与物大小；光屏不能接收虚像（实际光线未到达）。
+- **误差原因**：玻璃板与水平面不垂直；玻璃板有厚度，两个面反射成像（厚玻璃板可见两个像）。
+- **例题**：视力表距镜子3.5米，人距镜子1.5米可看到5米处虚像；视力表距镜子3米时人距镜子2米；人距平面镜1米时人与像距离2米，远离时像大小不变。
+- **易混点**：人在河边看到树的倒影是平面镜成像（正立等大虚像），*倒影是文学描述，并非倒立像*；河水深度比实际浅是光的折射。
 ## 球面镜及其应用
-- **凸面镜**：对光线起**发散作用**，成**正立、缩小的虚像**；应用于汽车后视镜、丁字路口反光镜。
-- **凹面镜**：对光线起**会聚作用**，平行光会聚于焦点 `F`；应用于手电筒电珠、汽车前大灯、探照灯、耳鼻喉科检查镜、太阳灶。
-- **太阳灶**：西藏藏民用凹面镜烧水，环保节能；北京因无场地架锅较少使用。
-- **以直代曲原则**：讨论球面镜作图时，将曲面看作许多小平面镜的组合。
-- **阿基米德传说**：曾组织妇女用平面镜围成凹面，会聚光线烧毁敌人帆船。
-- **玻璃幕墙隐患** ⭐：凹面玻璃幕墙会聚光线可**烧死树木**（如校园枣树三年枯死）、引燃电线，造成**光污染**和噪音反射。
+- **凸面镜**：对光线起**发散作用**，成正立、缩小的虚像；用于汽车后视镜、丁字路口拐弯处镜子。
+- **凹面镜**：对光线起**会聚作用**，焦点处可放光源；用于手电筒、汽车前大灯、探照灯、太阳灶、医生额镜（中间镂空便于观察）。
+- **历史与应用**：阿基米德组织妇女用平面镜围成凹面烧敌船；玻璃幕墙形成凹面会聚光线，可能烧死树木、引发火灾，属**光污染**。
 # 课堂互动与答疑
-**学生**：光在均匀介质中沿直线传播，那穿过整个大气层时还成立吗？为什么太阳看起来会“越出地平线”？
-**教师**：不成立。大气层越往外越稀薄，是不均匀介质，光线会发生偏折，所以太阳还没到地平线上时就能被看到；宇航员在月球上看太阳则必须沿直线。星星“眨眼睛”也是大气层不均匀造成的。
-**学生**：小孔成像成的像一定是倒立的吗？放大缩小怎么判断？
-**教师**：一定是倒立的实像，因为光线实际到达光屏；但放大缩小不一定，物体离孔越远、光屏离孔越近，像越小。像的形状与孔的形状无关，只取决于物体本身，如树荫下的圆形光斑就是太阳的像。
-**学生**：光垂直射到镜面上，入射角和反射角是多少度？
-**教师**：都是0度。入射角是入射光线与法线的夹角，垂直入射时光线与法线重合，夹角为0度，反射角也等于0度，不是90度。
-**学生**：入射光线与镜面夹角为40度时，入射角是多少？
-**教师**：50度。入射角是入射光线与法线的夹角，法线垂直于镜面，所以入射角＝90度－40度＝50度，反射角也等于50度。
-**学生**：画反射光线时，怎么保证角度准确？一定要用量角器吗？
-**教师**：不用量角器。先画法线（虚线，留作图痕迹），再在反射光线上找一个点，量出它到法线的距离，在法线另一侧对称位置取等距点，连接该点与入射点即可，利用等腰三角形保证反射角等于入射角。
-**学生**：镜面反射和漫反射都遵守光的反射定律吗？
-**教师**：都遵守。镜面反射是平行光射到光滑表面，反射光仍平行；漫反射是表面凹凸不平，把每个小面看作小平面镜，反射光射向各个方向。生活中大多数反射是漫反射，如黑板、电影银幕、人眼看到物体都靠漫反射。
-**学生**：雨后夜晚，迎着月光走和背着月光走，怎么判断哪里是水潭？
-**教师**：迎着月光走，亮处是水潭——水面发生镜面反射，反射光进入人眼；背着月光走，暗处是水潭——反射光射向另一侧，而地面发生漫反射反而更亮。可用手电筒照白纸上的小镜子验证：垂直照射时斜看，镜子是黑的，白纸是亮的。
-**学生**：平面镜成像实验中，为什么用玻璃板代替平面镜？
-**教师**：因为玻璃板既能反射成像，又能透过它看到后面的蜡烛，便于移动未点燃的蜡烛去确定像的位置；若用平面镜则无法看到后面，无法确定像的位置。
-**学生**：实验中蜡烛到玻璃板的距离与像到玻璃板的距离不相等，可能是什么原因？
-**教师**：一是玻璃板与水平面不垂直，导致像的位置偏移；二是玻璃板有厚度，前后两个面都能反射成像，若玻璃板较厚，会看到两个像，测量时产生误差。
-**学生**：平面镜成的像为什么是虚像？光屏能接收到吗？
-**教师**：不能。平面镜成像的原理是光的反射，反射光线的反向延长线会聚成虚像，实际光线并没有到达像的位置，所以光屏接收不到，手放到像的位置也不会被烫伤。
-**学生**：视力表距镜子3.5米，人距镜子多远才能看到5米远的虚像？
-**教师**：1.5米。视力表的像距镜子也是3.5米，人距镜子1.5米时，人到虚像的距离为3.5米＋1.5米＝5米，符合查视力要求的5米距离。
-**学生**：凸面镜和凹面镜对光线各起什么作用？成像有什么特点？
-**教师**：凸面镜对光线起发散作用，成像是正立、缩小的虚像，用于汽车后视镜、丁字路口反光镜，能看到更大范围；凹面镜对光线起会聚作用，平行光会聚于焦点，用于手电筒、汽车前大灯、太阳灶，焦点处可放置光源。
+**学生**：为什么研究反射时要引入法线，直接用量角器量入射光线和镜面的夹角不行吗？
+**教师**：法线是辅助线，垂直镜面、实际不存在。如果只研究反射，直接量夹角确实可行，但后面学折射时，入射角和折射角都必须以法线为基准来定义，所以现在引入法线是为折射做铺垫。
+**学生**：光垂直射到镜面上，入射角和反射角是多少？为什么不是90度？
+**教师**：都是0度。入射角的定义是入射光线与法线的夹角，垂直入射时光线与法线重合，夹角为0度，反射角也等于0度。容易误答成90度，是把入射角误当成光线与镜面的夹角了。
+**学生**：小孔成像为什么一定是倒立的实像？放大缩小怎么判断？
+**教师**：光沿直线传播，物体上方的光通过小孔落到光屏下方，所以像一定倒立；光线实际到达光屏，所以是实像。放大缩小取决于物距和像距的相对大小，物体远、光屏近则成缩小像，反之成放大像，与孔的形状无关。
+**学生**：月偏食和日偏食的形成区域一样吗？为什么月偏食不是月球处在半影区就算？
+**教师**：不一样。日食中月球在中间，2、3号半影区就是日偏食；月食中地球在中间，月球体积远小于地球，如果月球完全处于半影区，只是亮度略暗，不叫月偏食。月偏食必须是月球一部分在本影区（全黑）、一部分在半影区（仍亮）时才会出现。
+**学生**：画反射光线时，怎么快速找到对称位置，不用量角器量角度？
+**教师**：先画法线（虚线，留作图痕迹），再用刻度尺的刻度对准法线，在入射光线上找一个点，记下它到法线的距离，在法线另一侧等距处找对称点，连接入射点与该点即为反射光线，最后补全箭头。依据是反射角等于入射角，法线相当于角平分线。
+**学生**：雨后夜晚判断水潭位置，为什么迎着月光走亮处是水潭，背着月光走暗处是水潭？
+**教师**：水面发生镜面反射。迎着月光走，月光经水面反射后恰好进入人眼，所以水潭显亮；背着月光走，反射光朝反方向射出不进入人眼，而地面发生漫反射仍有部分光进入人眼，所以水潭反而比地面暗。
+**学生**：平面镜成像实验中，为什么用玻璃板而不用镜子？为什么能看到两个像？
+**教师**：用玻璃板是为了透过它看到后面的蜡烛，便于移动未点燃蜡烛来确定像的位置，用镜子则完全看不到后方。看到两个像是因为玻璃板有厚度，前后两个表面都能反射成像，玻璃板越厚两个像越明显，所以实验应选薄玻璃板。
+**学生**：平面镜成像实验中，测得蜡烛到玻璃板距离与像到玻璃板距离不相等，可能是什么原因？
+**教师**：两个原因：一是玻璃板与水平面不垂直，放置倾斜导致像的位置偏移；二是实验前画好的镜面位置线与实际放置的玻璃板没有重合，测量时按错误基准读数。
+**学生**：凸面镜和凹面镜对光线各起什么作用？分别用在哪些地方？
+**教师**：凸面镜对光线起发散作用，成正立缩小虚像，视野更大，用于汽车后视镜、丁字路口转弯镜；凹面镜对光线起会聚作用，平行光经反射会聚于焦点，用于手电筒、汽车前大灯、探照灯、太阳灶和医生额镜。
 # 课后任务与学习建议
 ## 课堂练习
-- **第1题**：考点为光在均匀介质中沿直线传播，结论是三点一线、影子、月全食均依据此原理。
-- **第2题**：激光从地球射到月球表面用时1.25秒，按真空光速3×10⁸米/秒计算，距离为3.75×10⁸米。
-- **第3题**：发生雷电时先看到闪电后听到雷声，原因是光速比声速快（声速约340米/秒）。
-- **第4题**：单选选C，光在均匀介质中沿直线传播；B项未强调真空，D项不同介质中光速不相同。
-- **第5题**：多选选BCD，属于光沿直线传播的现象；平面镜成像属于反射。
-- **第6题**：选ABC，D项错误在于必须强调均匀介质，光传播路线不能笼统说直线。
-- **第7题**：验证光的反射定律探究实验，用带刻度的硬纸板（中间用透明胶带粘合可前后转动）和小平面镜、激光笔，在家可自制。
-- **第8题**：作图题，画反射或入射光线时先画法线（虚线，两三段即可），再根据反射角等于入射角找对称点连线，最后补全箭头。
-- **第9题**：反射光线与平面镜夹角40度，则入射角为50度，选A。
-- **第10题**：入射光线与镜面夹角增大时，入射角减小、反射角也减小，传播速度不变，选C。
-- **第11题**：入射光线与法线夹角60度，反射角为60度。
-- **第12题**：反射光线与入射光线夹角80度，反射角为40度（角平分线）。
-- **第13题**：雨后夜晚，迎着月光走时发亮处是水潭（镜面反射），背着月光走时暗处是水潭。
-- **第14题**：选B，依据光路可逆原理；A项垂直入射反射角应为0度，C项漫反射也遵守反射定律，D项不同介质光速不同。
-- **第15题**：电影院白色银幕对光产生漫反射，选B。
-- **第16题**：教室某些位置看黑板只见光亮看不清粉笔字，是黑板发生镜面反射；电影银幕反射进入人眼是漫反射，两种反射都遵守反射定律。
-- **第17题**：电影院白色屏幕粗糙，为使射到屏幕上的光发生漫反射。
-- **第18题**：选D，人在河边看到岸边的树在水中的倒影属于光的反射；A、B为直线传播，C为折射。
-- **第19题**：平面镜成像实验中，蜡烛到玻璃板距离与像到玻璃板距离不相等，原因一是玻璃板与水平面不垂直，二是玻璃板有厚度、两个面反射成像。
-- **第20题**：用玻璃板代替镜子便于移动后方蜡烛确定像的位置；刻度尺用于比较像与物到镜面距离；两段完全相同蜡烛用于比较像与物大小；光屏不能接收到烛焰的像（虚像）；物体靠近玻璃板时像的大小不变。
-- **第21题**：视力表距镜子3.5米，像距镜子3.5米，人距镜子1.5米即可看到5米处的虚像。
-- **第22题**：视力表距镜子3米，人距镜子2米即可，选B。
-- **第23题**：人站在平面镜前1米处，人与像之间距离为2米。
-- **第24题**：人向远离平面镜方向移动，镜中像的大小不变，选C。
+- **练习1–5（直线传播）**：考点为光在均匀介质中沿直线传播；影子和月全食均据此解释，激光从地球到月球1.25秒，距离为3.75×10⁸米。
+- **练习4（直线传播）**：考点为光速与声速比较；发生雷电时先看到闪电后听到雷声，因光速比声速快，声速15℃时为340米/秒。
+- **练习5（直线传播）**：多选答案为bcd；平面镜成像属反射而非直线传播，D项漏掉「均匀介质」这一条件故不选。
+- **练习6（直线传播）**：答案为abc；D项只说「传播路线」未强调均匀介质，表述不严密。
+- **练习7（反射定律探究）**：考点为反射定律实验装置；用带刻度硬纸板（中间用透明胶带粘合可前后转动）＋小平面镜＋激光笔，可在家自制验证。
+- **练习8（反射作图）**：考点为反射光线作图；步骤为先画法线（虚线，留痕迹），再根据反射角等于入射角找对称点画入射光线，最后补全箭头。
+- **练习9（反射角计算）**：反射光线与平面镜夹角40°，则与法线夹角50°，入射角＝反射角＝50°，选a。
+- **练习10（反射角变化）**：入射光线与镜面夹角增大时，入射角减小、反射角也减小，传播速度不变，选C。
+- **练习11（反射角计算）**：入射光线与法线夹角60°时，反射角为60°。
+- **练习12（反射角计算）**：反射光线与入射光线夹角80°时，反射角为40°（角平分线）。
+- **练习13（雨后水潭判断）**：考点为镜面反射与漫反射；迎着月光走，发亮处是水潭（镜面反射），背着月光走，发暗处是水潭。
+- **练习14（光路可逆）**：a错（垂直入射反射角为0°非90°）；b对（光路可逆）；c错（漫反射也遵守反射定律）；d错（不同介质光速不同）。
+- **练习15（漫反射）**：电影院白色银幕对光产生漫反射，选b。
+- **练习16（反射类型判断）**：黑板反光看不清粉笔字是镜面反射；电影银幕反射进入人眼是漫反射；两种反射均遵守反射定律。
+- **练习17（漫反射）**：电影院白色屏幕粗糙是为了使光发生漫反射。
+- **练习18（反射现象判断）**：选d；人在河边看到岸边树的倒影是平面镜成像（反射），a、b为直线传播，c为折射。
+- **练习19（平面镜成像实验）**：考点为实验误差分析；玻璃板与水平面不垂直、玻璃板有厚度（两个面反射成像）均会导致数据异常或出现两个像。
+- **练习20（平面镜成像实验）**：玻璃板代替平面镜便于确定像的位置；刻度尺比较像与物到镜面距离；两段相同蜡烛比较像与物大小；光屏不能接收虚像；物体靠近玻璃板时像的大小不变。
+- **练习21（视力表）**：视力表距镜子3.5米，像距镜子3.5米，人距镜子1.5米即可看到5米处虚像。
+- **练习22（视力表）**：视力表距镜子3米，像距镜子3米，人距镜子2米即可，选2b。
+- **练习23（平面镜成像）**：人站在平面镜前1米处，人与像之间距离为2米。
+- **练习24（平面镜成像）**：人向远离平面镜方向移动，像的大小不变，选C。
 ## 复习重点
-- **光源**：自身能够发光的物体，分为自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
-- **光线**：带箭头的直线，是物理模型，并非真实存在；按来源分点光源和平行光源。
-- **光沿直线传播**：光在均匀介质中沿直线传播；大气层不均匀时光线发生偏折，故日出时太阳实际位置低于所见位置，星星闪烁也由此造成。
-- **小孔成像**：成倒立实像（光线实际到达），放大缩小不一定，与孔的形状无关；树荫下光斑是太阳经树叶缝隙形成的小孔成像。
-- **日食与月食**：日食时月球在太阳与地球之间，分日全食（1号区域）、日偏食（2、3号区域）、日环食（4号区域）；月食时地球在中间，月全食是月球完全进入地球阴影，月偏食是月球部分在1号区域、部分在2或3号区域。
-- **光速**：真空中为3×10⁸米/秒（3×10⁵千米/秒），一秒钟绕地球赤道约7圈半；空气中略慢（约2.99×10⁸米/秒），水中约为真空的3/4，玻璃中约为2/3。
-- **光的反射定律**：反射光线、入射光线和法线在同一平面内；反射光线和入射光线分居法线两侧；反射角等于入射角；垂直入射时入射角和反射角均为0度。
-- **镜面反射与漫反射**：镜面反射是平行光射到光滑表面反射光仍平行；漫反射是射到凹凸不平表面反射光射向各个方向；两者都遵守反射定律，生活中大多数反射是漫反射。
-- **平面镜成像**：成**正立、等大的虚像**，像与物到镜面距离相等、连线与镜面垂直；平静水面、光滑金属表面可充当平面镜。
-- **光路可逆**：若甲能看到乙在平面镜中的像，则乙也一定能看到甲在平面镜中的像。
-- **凸面镜**：对光线起发散作用，成正立、缩小的虚像，用于汽车后视镜、丁字路口反光镜。
-- **凹面镜**：对光线起会聚作用，焦点处可放光源，用于手电筒、汽车前大灯、探照灯、太阳灶、耳鼻喉科检查镜。
+- **光源**：自身能够发光的物体；按来源分为自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
+- **光线**：带箭头的直线，是物理模型，并非真实存在；按形状分为点光源（蜡烛）和平行光源（太阳）。
+- **光沿直线传播**：适用条件为均匀介质；大气层不均匀时光线发生偏折（日出、星星眨眼），月球上无大气层则沿直线看太阳。
+- **小孔成像**：成倒立实像（光线实际到达），放大缩小不一定，与孔形状无关；实例为树荫下光斑（太阳缩小的像）。
+- **日食与月食**：日食为太阳、月球、地球同一直线且月球在中间，分日全食（1号区）、日偏食（2、3号区）、日环食（4号区）；月食为太阳、地球、月球同一直线且地球在中间，月球完全在阴影中为月全食，部分在阴影中为月偏食。
+- **光速**：真空中3×10⁸米/秒（3×10⁵千米/秒），约一秒钟绕地球赤道7圈半；空气中略慢（近似2.99×10⁸米/秒），水中约为真空中的3/4，玻璃中约为2/3。
+- **光的反射定律**：反射光线、入射光线、法线在同一平面内（共面）；反射光线和入射光线分居法线两侧；反射角等于入射角；法线为辅助线，垂直镜面，不存在。
+- **垂直入射**：光垂直射到镜面上时，入射角与反射角均为0度（易错答成90度）。
+- **镜面反射与漫反射**：镜面反射为平行光射到光滑表面反射光平行；漫反射为表面凹凸不平、反射光向各个方向；两者均遵守反射定律；生活中大多数反射为漫反射（黑板、电影银幕、人眼看到物体）。
+- **平面镜成像**：原理为光的反射定律；特点为正立、等大、虚像，像与物关于镜面对称；平静水面、光滑金属表面可充当平面镜。
+- **凸面镜与凹面镜**：凸面镜对光线起发散作用，成正立缩小虚像（汽车后视镜、丁字路口镜）；凹面镜对光线起会聚作用，焦点处可放光源（手电筒、汽车前大灯、探照灯、太阳灶、医生额镜）。
 ## 学习建议
-- **自制小孔成像实验**：用纸杯或易拉罐底部用针扎小孔（不要用钉子杵大孔），前面蒙上塑料布，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像，体会与孔形状无关。
-- **自制反射定律实验**：用硬纸壳中间用透明胶带粘合可前后转动，画上均匀刻度格，放一面小平面镜，用激光笔照射即可在家研究反射定律。
-- **购买激光笔**：两元店或十元店即可买到装一节干电池的激光笔，光强度大、线直，适合研究直线传播和反射实验。
-- **吸管验证光沿直线传播**：用激光笔对准直吸管照射墙上可见光点，将吸管弯折后光点消失，证明光不会自行拐弯。
-- **手电筒验证镜面反射与漫反射**：白纸上放一面小镜子，手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的，因镜子发生镜面反射、白纸发生漫反射。
-- **平面镜成像实验**：垫白纸、立透明玻璃板，用两个蜡烛（或两枚跳棋子），移动后方未点燃蜡烛至像的位置，记录位置可验证像与物到镜面距离相等、连线垂直。
-- **观察生活中的面镜**：摸停车场拐角处的镜子判断凸凹，观察汽车后视镜中物体是正立缩小的虚像；网上搜索"太阳灶"图片了解凹面镜应用。
-- **保护眼睛**：主讲人提醒长时间盯屏幕、写字姿势不正、教室全天拉窗帘都伤眼，应多到户外让眼睛接触自然光。</t>
+- **自制小孔成像实验**：用纸杯底部拿针扎一个小孔（不要用钉子杵大孔），杯口蒙上塑料布，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像，体会像与孔形状无关。
+- **自制反射定律实验**：用硬纸壳（中间用透明胶带粘合可前后转动）＋小平面镜＋激光笔，在纸壳上画均匀刻度，可在家验证反射定律。
+- **自制镜面反射与漫反射对比实验**：白纸上放一面小镜子，用手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的，说明镜面反射与漫反射的区别。
+- **购买激光笔**：两元店或十元店即可买到，激光笔光线强度大、线直，适合研究直线传播和反射实验，不必买贵的。
+- **观察生活中的光学现象**：夏天观察大杨树底下的光斑（小孔成像）、雨后夜晚判断水潭位置（镜面反射）、停车场丁字路口凸面镜成像，均可巩固课堂知识。
+- **保护眼睛**：主讲人提醒长时间盯屏幕、写字姿势歪、教室长期拉窗帘等习惯会加速视力下降，建议多户外活动、减少用眼疲劳。</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>75.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25691/7419</t>
+          <t>25691/6407</t>
         </is>
       </c>
     </row>
@@ -4657,119 +4560,96 @@
       <c r="C13" t="inlineStr">
         <is>
           <t># 课程概况
-本课程为《电气工程基础》导论课，是电气类专业学生进入专业课的第一门入门课。主讲人首先阐明课程两大教学目标：掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与整体关系，建立电力系统整体概念；掌握电力系统分析、设计、运行、管理方面的基础理论、基本技术与基本计算方法。课程要求前修电路理论和电机学知识，特别是变压器和同步电机；后续重要课程包括电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。第一章为重点章节，涉及概念最多，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及对其要求，掌握电能质量指标及国家标准规定范围，了解中性点接地方式；学习难点包括电能不能大量储存决定的有功无功动态平衡、额定电压规定繁杂、中性点接地方式影响后续章节。
-主讲人随后梳理电力发展简史，从直流输电起步：1874年俄国工程师在彼得堡建成4.5公里直流线路（4.5千瓦）；1882年法国德普勒架设首条57公里直流试验线路（首端343伏、末端850伏、200瓦、损耗78%）；1883年14公里试验（1.1千瓦、损耗55%）；1882年英国发明直流三线制系统（外线与中线110伏、两外线间220伏）。直流输电受电压等级低损耗大、提高电压困难、大容量高压直流发电机难制造等限制；19世纪末法国方剑串联多台直流发电机将75千瓦送75千米，20世纪初瑞典科学家装短路器后20多年建15条直流线路，1906年投运法国慕尼黑至里昂180公里、57千伏、4700千瓦线路，1927年改建为260公里、125千伏、19000千瓦。交流输电方面，英国法拉第电磁感应原理、美国亨利多线圈变压器前身、1876年俄国单相变压器、1883年特斯拉感应电机、1885年匈牙利多台变压器并联运行；1886年威斯汀豪斯在美国麻省1000伏1.2千米交流示范，后建成17英里2千伏线路；1886年俄国发明三相交流电和三相异步电动机。交直流之争中，爱迪生与凯尔文主张直流（效率高、认为交流危险），威斯汀豪斯与特斯拉主张交流（易升压降压、减少损失）；从法国到德国的交流输电线路为重要标志，采用三相发电机、升压变压器，在法兰克福建两座降压变供照明和100马力三相异步电动机。交流输电随绝缘技术发展：1898年针式绝缘子（33千伏）、1906年悬式绝缘子（110千伏）、1912年铝线应用（154千伏）、1923年均压阀技术（220千伏）、1936年美国287千伏、1952年瑞典380千伏（首次分裂导线）、1956年苏联400千伏双回线、1965年加拿大735千伏、1969年美国765千伏、1985年苏联1150千伏（后降压500千伏）。国内：1941年220千伏、1972年330千伏、1981年500千伏、2009年1000千伏交流特高压投运。直流在联网中优势显现：1954年瑞典本土至哥特兰岛世界首个工业海底电缆（100千伏、96公里、汞弧阀），1970年扩建50千伏1万千瓦晶闸管换流阀试验工程，1972年加拿大世界首个晶闸管换流阀背靠背直流工程；中国首个直流工程为舟山群岛与浙江定海连接，1989年葛上直流（葛洲坝至上海，±500千伏），今年6月投运云广直流±800千伏特高压直流工程。主讲人推荐三本书供课后阅读。
-主讲人解释交流输电占主导地位的原因：三相交流系统具有三个优点——易于产生旋转磁场使三相电动机易做驱动、瞬时功率恒定不随时间变化、输电线路导线量（金属消耗量）最少。除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内大多数高压、超高压、特高压输电采用三相交流，联网时采用直流。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小，因此在交流输电领域得到广泛应用，目前仍采用。
-主讲人阐述电力系统形成过程：早期单机供电可靠性差，发电机出问题负荷即停电；通过并联发电机提高可靠性，一台出问题另一台可带重要负荷。输电线路有电阻和电抗，传输功率时产生电压损耗和功率损耗，距离不能太长；提高电压可减小电流，从而减小有功功率损耗和电压降落，使输电距离变长。交流升压采用变压器，一侧升压另一侧降压；近距离（几十到几百米）发电机可直接相连，远距离需升压传输。电力系统雏形为多台发电机共同供电，发电机数目足够多可保证供电；好处包括可装大机组、供电范围扩大、带来经济效益。远距离输电中间可装设变电站，降压向中间负荷供电，并解决稳定问题。现代电力系统为发电机发电、升压变压器升压、输电线路传输到负荷中心、降压后给用电设备。电力系统定义：由发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能；四个环节为发电、输电、配电、用电。电力网是去除发电机和用电设备的部分；动力系统是电力系统加上动力部分（火电锅炉汽机煤炭系统、水电水轮机水坝水库等）。
-主讲人介绍电网分类：按规模分为地方电力网、区域电力网、超高压远距离输送网络。地方电力网向固定地方供电，电压等级一般在110千伏及以下（早期定义35千伏及以下），供电半径20~50公里；区域电力网电压等级110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心；超高压远距离输送网络电压等级500千伏或1000千伏（东北有330千伏网络），主要任务是把发电厂电能送到负荷中心，构成跨省跨地区大型电力系统。实例：特高压系统从山西晋东南到湖北荆门，跨三个省，连接华北电网和华中电网，属于超高压远距离输送网络；武汉电网属于地方电力网，主要供电电压110千伏和35千伏，少数220千伏，供电半径一般在50公里以内；华中网是典型区域网，华中几省紧密联系；葛上直流、三峡到上海输电线路属于超高压远距离输电网络。随着电网发展，各级电网电压等级会提高，变电站地位也会变化。变电站分类方法一：按最高电压等级分类，如华工变电站10千伏变380伏为10千伏变电站，关山变电站最高电压220千伏为220千伏变电站，凤凰山变电站最高电压500千伏为500千伏变电站；分类方法二：按主要功率流通方向分为升压变电站和降压变电站，大部分功率从高压侧流向低压侧为降压变电站，发电厂中大部分功率从低压侧升到高压侧为升压变电站。
+电气工程基础是电气类专业进入专业课后的第一门入门课，本次课程为导论与第一章导学。主讲人首先阐明课程两大教学目标：掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与整体的关系，建立电力系统整体概念；掌握电力系统分析、设计、运行、管理方面的基础理论、基本技术和基本计算方法。课程前修要求为电路理论和电机学知识，特别是变压器和同步电机；后续重要课程包括电力系统分析、电力系统机电保护、电力系统自动化和高电压技术。
+第一章为概念最多、最重要的章节，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统的特点及对设计运行的影响，掌握电能质量指标及国家标准规定的范围，了解常用接地方式特别是中性点接地方式的不同特点。主讲人指出三个学习难点：电能不能大量储存决定的有功无功动态平衡问题、额定电压规定繁杂、各种中性点接地方式影响后续章节且学习困难，并给出学习方法建议：注意概念内涵外延、从特点要求出发推导、寻找额定电压规律、比较不同接地方式特点。
+课程主体内容围绕电力发展简史展开：直流输电从福泰勒2000米导线试验起步，经1874年俄国4.5公里线路、1882年德普勒57公里试验线路（首端电压343伏、末端850伏、输送功率200瓦、损耗78%）、1883年14公里试验（输送功率1.1千瓦、损耗55%），到19世纪末法国方剑串联直流发电机将75千瓦电力输送75千米，20世纪初瑞典科学家加装短路器后20多年建成15条直流线路，最大为1906年法国慕尼黑水电厂到里昂的180公里、57千伏、4700千瓦线路，1927年改建为260公里、125千伏、19000千瓦。交流输电方面，1883年特斯拉制造感应电机，1885年匈牙利科学家实现多台变压器并联运行，1886年威斯汀豪斯在美国麻省进行1.2千米30千伏交流输电示范，交直流电力战争以交流胜出，此后交流电压等级逐步提升至1936年美国287千伏、1952年瑞典380千伏（首次采用分裂导线）、1965年加拿大735千伏、1969年美国765千伏、1985年苏联1150千伏（后降压至500千伏运行）；国内1941年投运220千伏、1972年330千伏、1981年500千伏、2009年1000千伏交流特高压。直流输电复兴用于联网：1954年瑞典本土与哥特兰岛建成世界首个工业海底电缆直流工程（100千伏、96公里），1972年世界首个晶闸管换流阀背靠背直流工程在加拿大投运；中国首个直流工程为舟山群岛与浙江定海连接，1989年葛上直流（葛洲坝电厂到上海）±500千伏，近年投运云广直流±800千伏特高压直流工程。
+课程还讲解了交流输电占主导地位的原因（三相交流易于产生旋转磁场、瞬时功率恒定、输电线路金属消耗量最少；三相三线制传输效率最高），电力系统形成过程（从单机供电到多机互联，提高电压可减小电流、降低损耗、使输电距离变长），以及电网按规模分为地方电力网（110千伏及以下，供电半径20~50公里）、区域电力网（110、220千伏和少量500千伏，供电半径超过50公里）、超高压远距离输送网络（500千伏或1000千伏，东北有330千伏）三类，变电站按最高电压等级和主要功率流通方向分类。
 # 核心知识点梳理
-## 课程定位与学习目标
-- **课程性质**：电气工程基础是进入专业课后的**第一门入门课**，为专业学习奠定基础。
-- **教学目标一**：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念。
-- **教学目标二**：掌握电力系统在**分析、设计、运行、管理**方面的基础理论、基本技术与基本计算方法。
-- **前修课程**：要求具备电路理论和电机学知识，特别是**变压器和同步电机**相关知识要求较高，有欠缺的同学需自行补充。
+## 课程定位与教学目标
+- **课程定位**：电气工程基础是进入专业课后的**第一门入门课**，前修要求为电路理论和电机学知识，特别是**变压器和同步电机**相关内容要求较高。
+- **教学目标一**：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与电力系统整体之间的关系，建立电力系统整体概念。
+- **教学目标二**：掌握电力系统在**分析、设计、运行、管理**方面的基础理论、基本技术及基本计算方法。
 - **后续课程**：最重要的四门为电力系统分析、电力系统机电保护、电力系统自动化和高电压技术。
-## 第一章学习内容与难点
-- **基本概念**：需掌握电力系统、电力网、动力系统和变电站等基本概念，本章是全书概念最多、最重要的章节。
-- **电力系统特点**：理解电力系统的特点及其引起的设计运行基础理论，以及由此对电力系统提出的要求。
-- **电能质量指标**：掌握电能质量指标及**国家标准**规定的各种范围。
-- **接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地方式）的不同特点。
-- **难点一 ⭐**：由电力系统特点引出的基本原理，如**电能不能大量储存**决定了有功功率和无功功率的动态平衡问题，是运行调整和设计的基础。
-- **难点二 ⭐**：电力系统额定电压的规定繁杂，需注意寻找规定之间的基本规律。
-- **难点三 ⭐**：各种中性点接地方式直接影响后续多个章节内容，学习难度较大。
-- **学习方法**：基本概念注意内涵与外延并适当记忆；思考从电力系统特点和要求出发，从最基础原理推导，**不要死记结论**；比较不同中性点接地方式的特点。
-## 电力发展简史
-- **直流输电起源**：福泰勒用2000米导线连接瓦斯发电机，拖动直流发电机、电动机和带水泵的电动机，证明直流远距离输电可行。
-- **1874年**：俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率4.5千瓦，后用于有轨电车的最原始工业试验。
-- **1882年**：法国德普勒架设首条**57公里**直流试验线路，采用电报线传输，首端电压343伏、末端850伏，输送功率200瓦，**损耗78%**。
-- **1883年**：德普勒从法国南部进行14公里输电试验，输送功率1.1千瓦，从瓦利尔书店到巴黎56公里损耗55%。
-- **三线制系统**：1882年10月英国科学家发明直流输电三线制系统，外线与中线间电压110伏、两外线间220伏，后扩展到5根线形成直流无限制系统。
-- **直流输电限制**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难，限制远距离大容量输电。
-- **串联发电机试验**：19世纪末法国方剑将多台直流发电机串联提高电压，把75千瓦电力送75千米。
-- **短路器突破**：20世纪初瑞典科学家在串联直流发电机上装短路器，使任意发电机投切不停电，此后20多年建成**15条**直流输电线路。
-- **1906年**：投运法国慕尼黑水电厂至里昂线路，**180公里、57千伏、4700千瓦**，为当时规模最大；1927年改建为260公里、125千伏、19000千瓦，接入两座水电站。
-- **直流输电制约**：设备复杂、运行方式复杂、造价高、可靠性差。
-- **变压器前身**：英国法拉第提出电磁感应原理；美国亨利用多线圈做原边、少线圈做副边，实现高电压感应低电压。
-- **交流输电早期成果**：1876年俄国发明单相变压器（用于照明）；1883年特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行方式。
-- **交直流之争**：爱迪生与凯尔文主张直流（效率高、认为交流危险），甚至购买威斯汀豪斯交流发电机卖给监狱执行死刑以证明交流危险；威斯汀豪斯与特斯拉主张交流（易用变压器升压降压、减少损失）。
-- **1886年**：威斯汀豪斯在美国麻省进行1000伏1.2千米交流输电示范，后在意大利建成17英里2千伏线路；同年俄国科学家发明三相交流电和三相异步电动机。
-- **交流输电标志性工程**：从法国到德国的交流输电线路，采用三相发电机和升压变压器，在法兰克福建两座降压变，一座供展览会照明，另一座供**100马力**三相异步电动机带动人工瀑布离心泵。
-- **绝缘技术推动升压**：1898年发明针式绝缘子（美国加州33千伏）；1906年发明悬式绝缘子（110千伏）；1912年发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用（154千伏）。
-- **高压输电里程碑**：1923年均压阀技术应用建成220千伏线路；1936年美国287千伏投运；1952年瑞典建成380千伏线路并**首次采用分裂导线**；1956年苏联400千伏双回线路投运。
-- **超高压与特高压**：1965年加拿大735千伏；1969年美国765千伏并入电网；1985年苏联1150千伏特高压投运，后降压至500千伏运行。
-- **国内交流输电**：1941年220千伏投运；1972年330千伏；1981年500千伏；**2009年1000千伏交流特高压投运**，为国家标志性首次成果。
-- **直流输电复兴**：交流大电网稳定问题突出后，直流在联网中优势显现，用于电网与电网之间的连接。
-- **1954年**：瑞典本土与哥特兰岛建成**世界首个工业海底电缆**直流工程，100千伏、96公里，采用汞弧阀。
-- **1970年**：瑞典本土与哥特兰岛扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年加拿大投运世界首个晶闸管换流阀背靠背直流工程。
-- **中国直流工程**：首个直流工程连接舟山群岛与浙江定海；1989年葛上直流（葛洲坝至上海）**±500千伏**；今年6月投运云广直流**±800千伏**特高压直流工程。
-- **课后阅读**：主讲人推荐三本书供学生了解电力发展史，作为电气专业学生应了解电力发展的基本历史。
-## 三相交流输电的优势
-- **三相系统优点一**：易于产生旋转磁场，三相电动机容易做驱动。
-- **三相系统优点二**：瞬时功率恒定，不随时间变化。
-- **三相系统优点三**：输电线路导线量（金属消耗量）最少。
-- **应用范围**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内大多数高压、超高压、特高压输电采用三相交流，联网时才采用直流。
-- **效率比较**：三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小，因此在交流输电领域得到广泛应用，目前仍采用。
-## 电力系统的形成与定义
-- **早期供电方式**：一台发电机向附近负荷供电（如展览会照明、大楼照明），各发电机孤立运行，可靠性差——发电机出问题负荷即停电。
-- **并联提高可靠性**：将两台发电机并联，一台出问题时另一台可带重要负荷，连接越来越多形成网络。
-- **输电线路参数**：导线有电阻和电抗两个重要参数，传输功率时产生电压损耗和功率损耗，阻抗越大、电流越大损耗越大，因此输电距离不能太长。
-- **升压原理**：传输有功功率一定时，电压升高则电流减小，有功功率损耗（I²R）和电压降落（IZ）均减小，输电距离可变长。
-- **变压器作用**：交流升压采用变压器，一侧升压、另一侧降压，中间电压升高后距离损耗降低。
-- **电力系统雏形**：近距离（几十到几百米）发电机可直接相连，远距离需升压传输，多台发电机共同供电即形成电力系统雏形。
-- **电力系统好处**：可装大机组向大范围供电，供电范围扩大，直接带来经济效益。
-- **远距离输电**：中间可装设变电站降压向中间负荷供电，同时解决稳定问题，并可引接部分负荷。
-- **现代电力系统**：发电机发电→升压变压器升压→输电线路传输到负荷中心→降压后供给用电设备。
-- **电力系统定义**：由发电机、变压器、输电线路和用电设备构成的整体，完成电能**生产、输送、分配、消耗**四个职能，四个环节为发电、输电、配电、用电。
-- **电力网定义**：电力系统中去除发电机和用电设备的部分（变压器和输电线路构成的网络），比电力系统少了发电厂和用电设备。
-- **动力系统定义**：在电力系统基础上加上发电厂动力部分（火电的锅炉、汽机、煤炭输送处理系统；水电的水轮机、水坝、水库等）。
+## 第一章学习要求与难点
+- **学习内容**：掌握电力系统、电力网、动力系统和变电站等基本概念；理解电力系统的特点及由特点引起的设计运行基础理论；理解对电力系统提出的要求。
+- **学习内容**：掌握电能质量指标及**国家标准规定的范围**；了解常用接地方式，特别是中性点（中心点）接地方式的不同特点。
+- **难点一 ⭐**：电能不能大量储存，决定了电力系统**有功功率和无功功率的动态平衡问题**，是运行调整和设计的基础。
+- **难点二 ⭐**：电力系统额定电压的规定繁杂，需注意把额定电压规定搞清楚；难点三 ⭐ 为各种中性点接地方式，直接影响后续多个章节且学习困难。
+- **学习方法**：注意概念的内涵和外延并适当记忆；从电力系统的特点要求出发、从最基础原理推导，**不要记结论**；寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。
+## 直流输电发展简史
+- **早期试验**：福泰勒用**2000米**导线连接瓦斯发电机，拖动直流发电机和电动机，证明直流远距离输电可行；1874年俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率**4.5千瓦**。
+- **德普勒试验**：1882年架设首条**57公里**直流试验线路，采用电报线传输，首端电压**343伏**、末端**850伏**，输送功率**200瓦**、损耗**78%**；1883年从法国南部进行**14公里**输电试验，输送功率**1.1千瓦**、损耗**55%**。
+- **三线制与串联升压**：1882年10月英国科学家发明直流三线制系统（外线与中线间**110伏**、外线间**220伏**），后扩展至五线制；19世纪末法国方剑串联多台直流发电机，将**75千瓦**电力输送**75千米**。
+- **技术突破与局限**：20世纪初瑞典科学家在串联直流发电机上加装短路器，使任意发电机投切不停电，此后20多年建成**15条**直流输电线路；最大为1906年法国慕尼黑水电厂到里昂的**180公里、57千伏、4700千瓦**线路，1927年改建为**260公里、125千伏、19000千瓦**。
+- **制约因素**：直流输电设备复杂、运行方式复杂、**造价高、可靠性差**；电压等级低时损耗大、电压降落快，制造大容量高压直流发电机困难。
+## 交流输电发展与交直流之争
+- **早期技术**：英国法拉第提出电磁感应原理；美国亨利用多线圈做原边、少线圈做副边实现变压，为变压器前身；1876年俄国科学家发明单相变压器（主要用于照明）。
+- **关键节点**：1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器**并联运行**方式；1886年威斯汀豪斯在美国麻省进行**1.2千米、30千伏**交流输电示范，同年又在意大利建成17英里高压输电线路。
+- **交直流之争**：爱迪生与凯尔文主张直流电，理由是直流效率高、交流有危险性（曾购买威斯汀豪斯交流发电机卖给监狱执行死刑以证明危险性）；威斯汀豪斯与特斯拉主张交流电，理由是**变压器易升压降压、减少电能损失**。
+- **交流电压等级演进**：1898年发明针式绝缘子后美国加州达**33千伏**；1906年悬式绝缘子建成**110千伏**；1912年发现电晕临界电压与导线直径成比例，美国建成**154千伏**；1923年均压阀技术应用建成**220千伏**；1936年美国**287千伏**投运；1952年瑞典**380千伏**首次采用分裂导线；1965年加拿大**735千伏**；1969年美国**765千伏**；1985年苏联**1150千伏**特高压投运（后降压至**500千伏**运行）。
+- **国内交流发展**：1941年投运**220千伏**，1972年**330千伏**，1981年**500千伏**，2009年**1000千伏**交流特高压首次投运。
+## 直流输电复兴与联网应用
+- **工业应用**：1954年瑞典本土与哥特兰岛建成**世界首个**工业海底电缆直流工程，**100千伏、96公里**，采用汞弧阀换流；1972年世界首个晶闸管换流阀背靠背直流工程在加拿大投运。
+- **中国直流工程**：首个直流工程连接**舟山群岛与浙江定海**；1989年葛上直流（葛洲坝电厂到上海）**±500千伏**；近年投运云广直流**±800千伏**特高压直流工程。
+- **应用定位**：交流大电网规模扩大后稳定问题突出，直流在**电网与电网之间联网**中的优势逐渐显露，故直流主要用于联网。
+## 三相交流输电优势
+- **优点一**：三相交流易于产生旋转磁场，三相电动机容易做驱动。
+- **优点二**：瞬时功率恒定，不随时间变化。
+- **优点三**：输电线路所用导线量（金属消耗量）最少；三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小。
+- **应用现状**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内高压、超高压、特高压输电大多采用三相交流，联网时采用直流。
+## 电力系统形成过程
+- **单机供电阶段**：最早一台发电机向附近负荷供电（如展览会照明、大楼照明），发电机出问题负荷即停电，**供电可靠性差**。
+- **多机互联阶段**：将多台发电机并联连接，一台出问题时另一台可带重要负荷，可靠性提高；可装大机组、扩大供电范围、带来经济效益。
+- **输电距离限制**：输电线路有**电阻和电抗**两个重要参数，传输功率时产生电压损耗和功率损耗；阻抗越大、电流越大损耗越大，故输电线路不能太长。
+- **升压解决**：传输有功功率一定时，**电压升高则电流减小**，有功损耗（I²R）和电压降落（IZ）均减小，输电距离变长；交流升压采用变压器，一侧升压另一侧降压。
+## 电力系统基本概念
+- **电力系统定义**：由发电机、变压器、输电线路和用电设备构成的整体，完成电能**生产、输送、分配、消耗**四方面职能，由发电、输电、配电、用电四个环节组成。
+- **电力网定义**：电力系统中去除发电机和用电设备后，由**变压器和输电线路**构成的网络。
+- **动力系统定义**：电力系统加上发电厂动力部分（火电的锅炉、汽机、煤炭输送处理系统；水电的水轮机、水坝、水库等）。
+- **易混点**：*电力网、电力系统、动力系统*三个概念范围不同——电力系统比电力网多了发电机和用电设备，动力系统比电力系统多了动力部分；行业中最常用的是电力网和电力系统两个概念。
 ## 电网分类
-- **地方电力网**：向固定地方供电，电压等级一般在**110千伏及以下**（早期定义为35千伏及以下），供电半径20~50公里。
-- **区域电力网**：电压等级110、220千伏和少量500千伏，供电半径**超过50公里**，联系较多发电厂和负荷中心。
-- **超高压远距离输送网络**：电压等级500千伏或1000千伏（东北有330千伏网络），主要任务是把发电厂电能送到负荷中心，构成跨省跨地区大型电力系统。
-- **实例一**：武汉电网属于地方电力网，主要供电电压110千伏和35千伏，少数220千伏，供电半径一般在50公里以内。
-- **实例二**：华中网是典型区域电网，华中几省紧密联系，供电半径较大。
-- **实例三**：特高压系统从山西晋东南到湖北荆门，跨三个省，连接华北电网和华中电网，属于超高压远距离输送网络。
-- **实例四**：葛上直流、三峡到上海输电线路属于超高压远距离输电网络。
-- **发展趋势**：随着电网发展，各级电网电压等级会提高，变电站地位也会随之变化。
+- **地方电力网**：向固定地方供电，电压等级一般在**110千伏及以下**（早期定义35千伏及以下），供电半径**20~50公里**；实例为武汉电网（主要供电电压110千伏和35千伏，少数220千伏）。
+- **区域电力网**：电压等级**110、220千伏**和少量500千伏，供电半径**超过50公里**，联系较多发电厂和负荷中心；实例为华中电网。
+- **超高压远距离输送网络**：电压等级**500千伏或1000千伏**（东北有330千伏），任务是把发电厂电能送到负荷中心，构成跨省跨地区大型电力系统；实例为山西晋东南到湖北荆门的特高压系统（跨三省、连接华北与华中电网）、葛上直流、三峡到上海的输电线路。
 ## 变电站分类
-- **按最高电压等级分类**：以站内最高电压等级命名，如华工变电站10千伏变380伏为10千伏变电站；关山变电站最高电压220千伏为220千伏变电站；凤凰山变电站最高电压500千伏为500千伏变电站。
-- **按功率流通方向分类**：分为升压变电站和降压变电站——大部分功率从高压侧流向低压侧为**降压变电站**；发电厂中大部分功率从低压侧升到高压侧为**升压变电站**。
+- **按最高电压等级分类**：以站内最高电压命名，如华工变电站（10千伏变380伏）为**10千伏变电站**，关山变电站为**220千伏变电站**，凤凰山变电站为**500千伏变电站**。
+- **按功率流通方向分类**：大部分功率从高压侧流向低压侧为**降压变电站**；发电厂中大部分功率从低压侧升压到高压侧为**升压变电站**。
+- **发展趋势**：随着电网电压等级提高和容量增大，各级电网电压等级会提高，变电站在电网中所处地位也会变化。
 # 课堂互动与答疑
-**学生**：为什么我国电力系统主要采用交流三相三线制，而不是直流输电？
-**教师**：三相交流系统有三个优点：易于产生旋转磁场，便于三相电动机驱动；瞬时功率恒定，不随时间变化；同等功率和功率因数下输电线路金属消耗量最少。三相三线制在各类传输方式中传输效率最高，因此除室内配电等小功率场合采用单相交流外，其余基本采用三相交流。直流主要用于电网间联网，如葛上直流±500千伏、云广直流±800千伏特高压工程。
+**学生**：为什么我们国家采用交流输电，而且用三相三线制，不用直流？
+**教师**：三相交流有三个优势：易于产生旋转磁场、瞬时功率恒定、输电线路金属消耗量最少。三相三线制在同等功率和功率因数下传输效率最高、导线金属消耗量最小，因此除室内配电等小功率场合用单相外，其余基本都用三相交流；国内高压、超高压、特高压输电均采用三相交流，只有电网联网时才用直流。
 **学生**：电力系统、电力网和动力系统这三个概念有什么区别？
-**教师**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配、消耗四个职能；电力网是电力系统中去除发电机和用电设备后的部分，即变压器和输电线路构成的网络；动力系统则是在电力系统基础上再计入发电厂动力部分，如火电厂的锅炉、汽机及煤炭输送系统，水电厂的水轮机、水坝、水库等。行业中最常用的是电力网和电力系统两个概念。
-**学生**：地方电力网、区域电力网和超高压远距离输送网络如何区分？
-**教师**：地方电力网向固定地区供电，电压等级一般在110千伏及以下（早期定义为35千伏及以下），供电半径20～50公里，如武汉电网；区域电力网电压等级为110、220千伏及少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心，如华中电网；超高压远距离输送网络电压等级为500千伏或1000千伏（东北有330千伏），主要任务是将发电厂电能远距离送至负荷中心，构成跨省跨地区大型电力系统，如晋东南至荆门特高压工程、三峡至上海输电线路。
+**教师**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能的生产、输送、分配和消耗；电力网是电力系统中去除发电机和用电设备后、由变压器和输电线路构成的网络；动力系统则在电力系统基础上再加入发电厂动力部分，如火电厂的锅炉、汽机、煤炭输送系统，水电厂的水轮机、水坝、水库等。行业中最常用的是电力网和电力系统两个概念。
+**学生**：地方电网、区域电网和超高压远距离输送网络怎么区分？
+**教师**：按电压等级和供电半径区分：地方电力网电压在110千伏及以下（早期定义35千伏及以下），供电半径20～50公里，如武汉电网；区域电力网电压为110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心，如华中电网；超高压远距离输送网络电压为500千伏或1000千伏（东北有330千伏），任务是把电能送到负荷中心，构成跨省跨地区大型电力系统，如山西晋东南到湖北荆门的特高压系统、葛上直流、三峡到上海的输电线路。
 **学生**：变电站按什么标准分类？
-**教师**：常见分类方法有两种。一是按最高电压等级分类，如华工变电站10千伏变380伏为10千伏变电站，关山变电站最高电压220千伏为220千伏变电站，凤凰山变电站最高电压500千伏为500千伏变电站。二是按主要功率流通方向分类：大部分功率从高压侧流向低压侧的为降压变电站；发电厂中大部分功率从低压侧升到高压侧的为升压变电站。
+**教师**：常见三种分类方法。按最高电压等级分类，如华工变电站10千伏变380伏为10千伏变电站，关山变电站最高电压220千伏为220千伏变电站，凤凰山变电站最高电压500千伏为500千伏变电站；按主要功率流通方向分为升压变电站和降压变电站，大部分功率从高压侧流向低压侧为降压变电站，发电厂中大部分功率从低压侧升压到高压侧为升压变电站。
 # 课后任务与学习建议
-## 课堂练习
-未提及
 ## 复习重点
-- **电力系统四个环节**：发电、输电、配电、用电的构成与工作原理，以及各环节与电力系统整体之间的关系，需建立电力系统整体概念。
-- **电力系统、电力网、动力系统定义**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配、消耗；电力网为去除发电机和用电设备的部分；动力系统为电力系统加上动力部分（火电锅炉汽机煤炭系统、水电水轮机水坝水库等）。
-- **电力系统特点引出的基本原理**：电能不能大量储存，决定有功功率和无功功率的动态平衡问题，是电力系统运行调整和设计的基础。
-- **电能质量指标**：掌握国家标准对电能质量指标规定的各种范围。
-- **额定电压规定**：电力系统额定电压的规定繁杂，需注意寻找规定之间的基本规律，注意使用条件变化时结论可能失效。
-- **中性点接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地）方式的不同特点，直接影响后续多个章节内容。
-- **三相交流输电优势**：三相系统易于产生旋转磁场、瞬时功率恒定、导线金属消耗量最少；三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小。
-- **电网分类**：地方电力网（110千伏及以下，供电半径20~50公里）、区域电力网（110、220千伏和少量500千伏，供电半径超50公里）、超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，跨省跨地区）。
-- **变电站分类**：按最高电压等级分类（如10千伏、220千伏、500千伏变电站）；按主要功率流通方向分为升压变电站和降压变电站。
+- **电力系统四个环节**：发电、输电、配电、用电的构成与工作原理，以及各环节与电力系统整体的关系，需建立电力系统整体概念。
+- **电力系统、电力网、动力系统定义**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配、消耗；电力网为电力系统中去除发电机和用电设备后的网络（变压器＋输电线路）；动力系统在电力系统基础上计入发电厂动力部分（锅炉、汽机、水轮机、水坝水库等）。
+- **电能质量指标**：掌握国家标准对电能质量指标规定的各种范围，属于第一章重点内容。
+- **电力系统特点及影响**：理解电力系统特点及其引起的设计、运行方面基础理论，如电能不能大量储存决定了有功功率和无功功率的动态平衡问题，是运行调整和设计的基础。
+- **额定电压规定**：电力系统额定电压的规定繁杂，需注意寻找规定之间的基本规律，不要死记结论。
+- **中性点接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地方式）的不同特点；该内容直接影响后续多个章节，学习难度较大。
+- **三相交流优势**：三相交流易于产生旋转磁场（三相电动机易做驱动）、瞬时功率恒定不随时间变化、输电线路金属消耗量最少；三相三线制传输效率最高，金属消耗量在同等功率和功率因数下最小。
+- **电网分类**：地方电力网电压等级110千伏及以下（早期定义35千伏及以下）、供电半径20~50公里；区域电力网电压等级110、220千伏和少量500千伏、供电半径超过50公里；超高压远距离输送网络电压等级500千伏或1000千伏（东北有330千伏），构成跨省跨地区大型电力系统。
+- **变电站分类**：按最高电压等级分类（如10千伏变电站、220千伏变电站、500千伏变电站）；按主要功率流通方向分为升压变电站（发电厂中大部分功率从低压侧升压到高压侧）和降压变电站（大部分功率从高压侧流向低压侧）。
 ## 学习建议
-- **补充前修知识**：对电路理论和电机学知识有欠缺的同学，应下去补充相关内容，特别是变压器和同步电机的相关知识，本课程要求较高。
-- **掌握基本概念方法**：对基本概念注意其内涵和外延，并适当结合实际；从电力系统的特点和要求出发，从最基础原理推导，不要死记结论。
-- **梳理额定电压规律**：注意寻找额定电压规定之间的基本规律，避免因规定繁杂而混淆。
-- **比较接地方式特点**：注意比较各种不同中性点接地方式之间的特点，为后续章节学习打基础。
-- **课后阅读电力发展史**：作为电气专业学生应了解电力发展的基本历史，主讲人推荐三本书供课后阅读，进一步了解交直流输电发展脉络。</t>
+- **补充前修知识**：对电路理论和电机学知识有欠缺的同学，特别是变压器和同步电机相关内容，应课后做一定补充，本课程对此要求较高。
+- **概念学习方法**：对基本概念注意其内涵和外延，并适当结合实际；从电力系统的特点和要求出发，从最基础原理推导，不要只记结论——使用条件变化时结论可能失效。
+- **额定电压学习**：注意寻找额定电压规定之间的基本规律，避免死记硬背繁杂规定。
+- **接地方式比较**：注意比较各种不同中性点接地方式之间的特点，为后续章节学习打基础。
+- **课外阅读**：作为电气专业学生应了解电力发展基本史，主讲人推荐三本书供课后阅读，了解交直流输电发展历程。
+- **结合实例理解**：通过实际例子对比理解电网分类，如武汉电网属地方电力网、华中电网属区域电网、葛上直流和三峡到上海输电线路属超高压远距离输送网络。</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>109.6</v>
+        <v>94.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11163/8593</t>
+          <t>11163/6925</t>
         </is>
       </c>
     </row>
@@ -4850,64 +4730,71 @@
       <c r="C14" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本期视频是皮卡新系列“评论”的试水之作，围绕Stack Exchange上关于调和级数∑1/n收敛性的经典问题展开。皮卡先为不懂微积分的观众介绍了级数收敛与发散的定义：收敛指存在固定实数a使所有部分和sn&lt;a，发散指存在无界递增的下界bn使sn&gt;bn。随后他逐一评论了网友的多种证明方法，并补充了柯西凝聚判别法、积分估计、差分法等思路，认为部分证明是事后凑出来的，不够自然。
-皮卡首先展示了网友的分组证明：将项按1、1/2+1/3、1/4~1/7、1/8~1/15等分组，每组和大于1/2，因此部分和无上界，故发散。他指出这一思路与柯西凝聚判别法的证明完全一致，并补充了该判别法的一般形式：非负不增序列的收敛性与∑2^k a_{2^k}相同。他还联想到高斯小时候1+2+…+100的分组求和，认为分组求和的思路在数学中很普遍。
-第二个证明是hn&gt;log(n+1)，皮卡指出log无上界，故hn发散。他介绍了三种流派：积分估计（用矩形面积近似hn，矩形面积大于曲边梯形面积）、差分法（利用e^{1/k}&gt;1+1/k，连乘积得到n+1）、以及Stolz定理（证明hn/log n的极限为1）。皮卡认为差分法（取对数、连乘积）是“事后凑出来的”，因为作者先知道结果再反推；Stolz定理同样“先射靶后画箭”，不够自然。他最后表示，如果反响不错，会继续出下一期评论其他帖子。
+本栏概括皮卡在视频中对Stack Exchange上调和级数∑1/n收敛性问题的评论。视频围绕调和级数发散这一经典结论，先介绍收敛与发散的定义，再逐一评点网友的多种证明方法，并补充柯西凝聚判别法、积分估计、差分法等数学工具。皮卡认为调和级数发散，但部分证明方法（如差分法）是事先知道结果后凑出来的，缺乏自然性。
 # 核心概念
 ## 调和级数的收敛与发散
 - **收敛定义**：对于正向级数，若存在**固定实数a**，使得所有部分和sn都小于a（无论n取多大），则称级数收敛。
-- **发散定义**：若存在无界递增的下界bn，使得sn&gt;bn，且bn可任意增大，则级数发散。
-- **调和级数**：∑1/n = 1+1/2+1/3+…+1/n，其部分和记为hn，是经典的发散级数。
-## 分组证明法
-- **核心思路**：将调和级数的项按1、1/2+1/3、1/4~1/7、1/8~1/15等分组，每组和均大于1/2。
-- **推演过程**：1/2+1/3&gt;1/4+1/4=1/2；1/4~1/7均大于1/8，4个1/8之和=1/2；1/8~1/15均大于1/16，8个1/16之和=1/2。
-- **结论**：级数包含任意多组，每组和大于1/2，故部分和无上界，级数发散。
+- **发散定义**：若存在一个**无界递增的下界bn**，使得sn大于bn，且bn可随n增大而无限增大，则级数发散。
+- **调和级数**：∑1/n = 1 + 1/2 + 1/3 + … + 1/n，其部分和记为hn，是**调和序列的部分和**；调和在英文中为`harmonic`。
+- **结论**：调和级数是**发散**的，因为log(n+1)无上界，而hn &gt; log(n+1)。
+## 分组求和证明
+- **核心思路**：将调和级数的项按组划分，每组和均大于1/2，从而证明整体发散。
+- **分组方式**：第1组为1，第2组为1/2+1/3，第3组为1/4+1/5+1/6+1/7，第4组为1/8到1/15，依此类推。
+- **关键估计**：每组中每项都大于该组项数的倒数（如1/4、1/3均大于1/4），因此每组和大于1/2。
+- **推演**：级数包含任意多组，每组和大于1/2，故任意多个1/2相加无上界，级数发散。
 ## 柯西凝聚判别法
-- **定义**：对于非负不增序列an，级数∑an的收敛性与∑2^k·a_{2^k}相同。
-- **证明思路**：与分组证明法完全一致，通过分组估计部分和。
-- **应用**：将调和级数转化为∑2^k·(1/2^k)=∑1，无穷个1相加无上界，故发散。
-- **意义**：适用于增长缓慢、不易直接判断收敛性的级数。
+- **定义**：对于**非负不增序列**，其收敛性与∑2^k·a_{2^k}的收敛性相同。
+- **证明思路**：与分组求和证明**完全一致**——分组后对每组做上界或下界估计，转化为对部分和的整体估计。
+- **应用价值**：适用于增长缓慢、不易直接判断收敛性的序列，如将∑1/n转化为∑2^k·(1/2^k) = ∑1，显然发散。
+- **推广**：皮卡推测柯西当年正是将分组求和思想推广到一般非负不增序列的和上。
+## 高斯求和的分组思想
+- **经典案例**：高斯幼年计算1+2+3+…+100，采用1+100=101、2+99=101的配对方式，只需数有多少个101。
+- **一般化**：若在求和中发现具有良好性质（满足估计要求、和恒定或有某种模式）的组，问题即可简化为对每组求和或估计，最后只需数组的个数。
 ## 积分估计法
-- **核心思想**：用积分曲线面积近似hn，矩形面积（高为1/n、底为1）始终大于曲边梯形面积。
-- **推演**：hn&gt;∫₁ⁿ⁺¹(1/x)dx = log(n+1)，而log无上界，故hn发散。
-- **流派定位**：属于较正规的积分收敛流派，与差分法、Stolz定理法并列为三种证明路径。
-## 差分法（取对数连乘积）
-- **核心步骤**：对e^{hn}取对数，利用e^{a+b}=e^a·e^b将和转化为连乘积。
-- **关键不等式**：e^{1/k}&gt;1+1/k，连乘积∏(1+1/k)相邻项相消，结果为n+1。
-- **皮卡评价**：认为此法**是事后凑出来的**——作者先知道hn&gt;log(n+1)的结果，再反向构造证明，属于“变魔术”式的障眼法。
-## Stolz定理法
-- **定理内容**：求形如an/bn（分子分母均趋于无穷大）的极限时，可考虑其差分(an+1-an)/(bn+1-bn)的极限。
-- **应用**：证明hn/log n的极限为1，差分后分子为1/(n+1)，分母为log(1+1/n)，极限为1。
-- **皮卡评价**：认为此法**不自然**，属于“先射靶后画箭”——事先知道hn满足log n的不等式才选择除以log n，若不知结果不可能凭空猜出log n。
+- **核心思想**：用积分曲线下的面积近似hn，进行放缩。
+- **几何解释**：hn从几何上可看作一系列矩形面积之和（高为1/n、底为1），这些矩形始终大于下方曲边梯形面积。
+- **推演**：∫₁ⁿ⁺¹ (1/x)dx = log(n+1)，故hn &gt; log(n+1)，而log无上界，因此级数发散。
+- **评价**：皮卡认为这是**较正规的流派**，但指出其中包含大量细节（见笔记中「和的积分估计」部分）。
+## 差分法（Stolz定理）
+- **方法**：用`Stolz定理`（中文常称`施托尔茨定理`）证明hn/log n → 1，从而说明hn与log n同增长级别，log n无上界故hn发散。
+- **差分计算**：分子差分hn+1 - hn = 1/(n+1)，分母差分log(n+1) - log n = log(1+1/n)，两者之比极限为1。
+- **皮卡评价**：该方法**不自然**，是**先射箭后画靶**——因事先知道hn满足log n的不等式，才选择除以log n；若不知结果，没有理由不选log log n²或√n。
+- **适用条件**：Stolz定理适用于分子分母均为无穷大的形如an/bn的极限问题，可通过差分极限间接求原极限。
+## 网友证明hn &gt; log(n+1)的指数法
+- **核心步骤**：对hn两边取指数，利用e^(a+b) = e^a·e^b将和转化为连乘积。
+- **关键不等式**：e^(1/k) &gt; 1 + 1/k，该不等式源于e^x &gt; 1+x，通常需微积分证明，但也可用(1+1/k)^k &lt; e的中学不等式替代。
+- **连乘积化简**：∏(1+1/k) = ∏(k+1)/k，相邻项相消后等于n+1。
+- **皮卡评价**：该方法**纯粹是装、变魔术**——通过障眼法让简单事实显得神奇，本质与对数差分法完全一致，只是两边取对数的不同写法。
 # 核心结论
 ## 核心结论
-- **调和级数∑1/n发散**：这是Stack Exchange上的经典问题，对学过高等数学的大学生是简单结论，但皮卡指出数学传播困难，民科吧曾有人反驳调和级数收敛并引发永无止境的论战。
-- **收敛定义**：对正向级数，若存在固定实数a，使所有部分和sn&lt;a（n取任意正整数），则级数收敛；若做不到，则发散。
-- **发散定义**：若能证明sn大于某个单向递增且永无止境的下界bn（任意给定多大数b，总可通过增大n使bn&gt;b），则级数发散。
-- **网友分组证明**：将项按1、1/2+1/3、1/4~1/7、1/8~1/15等分组，每组和大于1/2，部分和包含任意多组，故无上界、发散。
-- **柯西凝聚判别法**：对非负不增序列，其收敛性与∑2^k·a_{2^k}相同；证明思路与分组法完全一致，只需数有多少组（组数mn无界即可）。
-- **第二个证明hn&gt;log(n+1)**：log无上界，故hn发散；该证明有三种流派——积分估计、差分法、Stolz定理。
-- **积分估计流派**：hn从几何上约等于矩形面积，矩形始终大于下方曲边梯形，故hn大于∫1/x dx=log x的定积分，从而得到下界。
-- **差分法流派**：利用e^{1/k}&gt;1+1/k，连乘积相邻项相消得到n+1，从而证明hn&gt;log(n+1)；皮卡认为这是「事后凑出来的」，本质与对数差分不等式是一回事。
-- **Stolz定理流派**：证明hn/log n的极限为1，分子差分得1/(n+1)，分母差分得log(1+1/n)，两者求极限为1；皮卡认为这是「先射靶后画箭」，因为作者事先知道hn满足log n&lt;hn&lt;log n+1的不等式。
+- **调和级数发散**：∑1/n 的部分和 hn 无上界，故级数发散；这是微积分中的经典结论，对学过高等数学的大学生而言是基础题。
+- **收敛定义**：正向级数 ∑an 收敛，当且仅当存在固定实数 a，使所有部分和 sn 均小于 a（n 取任意正整数，包括 10 的 10 次方的 10 次方等极大值）。
+- **发散定义**：若存在无界递增的下界 bn，使 sn 恒大于 bn，且 bn 随 n 增大可超过任意给定数 b，则级数发散。
+- **分组求和证明**：将调和级数分组为 {1}、{1/2+1/3}、{1/4+1/5+1/6+1/7}、{1/8+…+1/15} 等，每组和均大于 1/2；因组数无限，部分和可超过任意上界，故发散。
+- **柯西凝聚判别法**：对非负不增序列 an，∑an 的收敛性与 ∑2^k·a_{2^k} 相同；其证明思路与分组求和完全一致，即分组后对每组做上下界估计。
+- **凝聚判别法应用**：对调和级数，∑2^k·(1/2^k)=∑1，即无穷个 1 相加，显然无上界，故发散；该方法适用于增长缓慢、不易直接判断收敛性的序列。
+- **hn&gt;log(n+1) 证明**：调和数 hn 大于 log(n+1)，因 log 函数无上界，故 hn 无上界，级数发散；log 在美国记作 log，在欧洲记作 ln，中国沿用欧洲记法。
+- **积分估计法**：hn 从几何上可看作矩形面积之和，每个矩形（高 1/n、底 1）始终大于下方曲边梯形面积，故 hn 大于 ∫₁ⁿ⁺¹(1/x)dx=log(n+1)；该流派被认为较正规。
+- **差分法结论**：用 Stolz 定理（中文亦称斯托尔兹定理）证明 hn/log n→1，因 log n 无上界，故 hn 发散；该方法适用于分子分母均为无穷大的比值极限问题。
+- **差分法不自然**：皮卡认为差分法是「先射箭后画靶」——因事先知道 hn 满足 log(n+1) 的不等式，才去凑 log n 作分母；若不知道结果，没有理由不选 log log n 的平方或根号 n 来尝试。
 ## 易混点与适用边界
-- **收敛与发散的判断标准**：收敛要求所有部分和sn都小于某个固定实数a（上界）；发散则要求存在无界递增的下界bn，两者是互补判断，不能混淆。
-- **柯西凝聚判别法的适用条件**：仅适用于**非负不增**序列；对增长很慢、不易直接判断收敛性的级数有本质帮助，如将∑1/n转化为∑1（无穷个1相加显然发散）。
-- **积分估计的几何前提**：hn的矩形面积始终大于曲边梯形面积，这一放缩方向是固定的；若方向反了则无法得到下界。
-- **差分法的前提**：e^{1/k}&gt;1+1/k这一不等式本身需要微积分或中学已知结论支撑；皮卡指出若不用微积分，需先证明(1+1/k)^k&lt;e，操作更复杂。
-- **Stolz定理的适用条件**：适用于分子分母均为无穷大的形如an/bn的极限问题，通过比较差分an+1−an与bn+1−bn的极限来间接求原极限；但皮卡强调，不知道hn变化率时不可能凭空蒙出log n，需先通过计算数据（如欧拉算几十项）才能猜测。
-- **常见误区**：皮卡认为取对数、连乘积的证明「纯粹就是装」，是作者先知道结果再反推凑出来的，会妨碍理解但让人感觉magic；Stolz定理同样「不自然」，属于先知道答案再选方法。
+- **收敛与发散判定**：收敛要求所有部分和 sn 小于某个固定实数 a（上界存在）；发散则要求存在无界递增的下界 bn，使 sn 恒大于 bn——两者互为否定，判定时只需验证其一。
+- **柯西凝聚判别法适用条件**：仅适用于**非负且不增**的序列 an；对一般序列不保证成立，使用时需先确认序列满足该前提。
+- **积分估计的几何边界**：hn 的矩形面积和始终大于积分 ∫₁ⁿ⁺¹(1/x)dx，是因为每个矩形（高 1/n、底 1）都覆盖在曲线 y=1/x 上方；若改用其他函数或区间，需重新验证放缩方向。
+- **差分法需预先知道结果**：Stolz 定理本身是有效的数学工具，但用它证明 hn/log n→1 时，必须先猜出 log n 这个分母；皮卡认为这属于「先知道答案再凑证明」，缺乏自然性。
+- **e^x&gt;1+x 不等式的微积分依赖**：该不等式本身需用微积分证明，而微积分建立在极限之上；皮卡指出若不用微积分，可改用 (1+1/k)^k&lt;e 的不等式链来操作，但用微积分更简单。
+- **调和数符号约定**：hn 是 1+1/2+…+1/n 的专用符号，因该序列称为调和序列的部分和；英文中调和为 harmonic，与「hard」谐音相关。
+- **log 记法差异**：美国记作 log，欧洲记作 ln，中国沿用欧洲记法；两者表示同一函数，不因记法不同而改变性质。
 ## 待澄清问题
-- **后续内容留待下期**：皮卡表示「后面还有很多方法，我们有机会再评论」，并提到若反响不错会出下一期，再找帖子或网友投稿来评论。
-- **dialectic分解思路未展开**：皮卡提到第一个证明背后还有dialectic分解的思路，但表示「一时半会也讲不清楚，这个视频时长可能就要超了」，未作详细说明。</t>
+- **后续视频计划**：皮卡表示后面还有很多证明方法，若本期反响不错，将出下一期再找帖子评论；若反响持续良好，会看网友投稿的解题思路进行评论。</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>40.1</v>
+        <v>38.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7465/3140</t>
+          <t>7465/3455</t>
         </is>
       </c>
     </row>
@@ -4970,66 +4857,77 @@
       <c r="C15" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本期内容由工作室老李主讲，围绕GitHub这一开源资源平台，系统介绍其作为资源库的价值、多个实用热门项目，以及国内用户访问与使用GitHub时常遇问题的解决方法。视频覆盖工作性价比评估、表情包合集、健康指南、证件照制作、自重健身、教材下载、AI视频生成、声音克隆、AI学习资源库与AI应用合集等十余个项目，并穿插现场演示与效果评价。
-针对网络不通、页面全英文、原生搜索不好用三大痛点，老李依次给出使用Watt Toolkit加速软件、GitHub镜像站（如gh-proxy）、VPN（魔法）三种访问方案，以及安装浏览器翻译插件或汉化插件解决语言问题，并推荐用ChatGPT等AI工具进行中文搜索以替代精准匹配的原生搜索。此外，还讲解了GitHub项目主页的构成要素（watch/fork/star、about、release、readme），提醒通过查看最近commit日期判断项目是否已停止维护，并介绍通过explore的trending查看全站热门项目的方法。
+本期视频由工作室老李主讲，围绕GitHub这一全球开源资源平台展开，核心议题是介绍平台上实用热门项目，并解决国内用户访问、汉化与搜索等常见问题。内容覆盖工作性价比评估、表情包博物馆、健康指南、一键证件照制作、健身教程、教材资源、AI视频生成、声音克隆、AI学习资源库及Awesome AI Apps等十余个项目，并穿插与小李的互动。针对国内访问困难，老李介绍了Watt Toolkit加速软件、镜像站与魔法（VPN）三种方案；同时讲解了注册、汉化插件安装、AI辅助搜索及项目主页功能（watch/fork/star、readme、commit日期）等使用技巧。整体基调为实用导向，面向普通用户降低GitHub使用门槛。
 # 核心概念
-## GitHub 资源库定位
-- **GitHub** 被定位为「巨大的宝藏资源库」，几乎能找到资源、教程、工具，涵盖名校公开课、大厂面试题、开源大模型、AI 学习资料等正经内容，也包括表情包合集、养生指南、大厂黑名单等非正经内容。
-- 项目以 `star` 数体现「江湖地位」，star 越多代表项目越受欢迎，是衡量项目热度的重要指标。
-## 实用热门项目
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等，综合给出工作性价比分数和评级；老李测试程序员工作，评估结果为「性价比还不错，优质牛马」。
-- **表情包博物馆**：收录国内过去多年全网爆火的表情包大合集，涵盖甄嬛传、罗翔老师、特朗普、马保国等主题，可用于斗图。
-- **健康指南项目**：分享经科学研究的健康知识，如间歇性进食促进胆汁代谢与炎症自愈、吃天然发酵类食品改善肠道菌群生态，目标是「活到 150 岁」。
-- **一键做证件照项目**：上传大头照即可一键抠图换背景，生成不同标准的证件照和各类规格打印模板。
-- **自重健身教程项目**：选择要练习的肌肉群后提供参考动画，适合请不起真人教练的用户，属于「丐版健身教练」。
-- **教材资源项目**：收集国内所有小学、初中、高中及部分大学的 PDF 教材，全部免费使用。
-- **全自动视频生成项目**：名为 `Morning Printer Turbo`，属于近期热门项目。
-- **声音克隆模型 `ChatBox TTS`**：零样本语言克隆，情感控制到位，克隆声音接近真人；上传自己的音频即可合成指定英文台词。
-- **AI 学习资源库**：涵盖大语言模型、`RAG`、`AI Agents`、`MSI` 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
-- **`Awesome AI Apps` 项目**：收录大模型最新 Agent 应用，如医学影像数据分析、AI 投资、竞争对手情报分析等，适合跟进 AI 应用落地案例或寻找创业点子。
-## GitHub 访问与使用技巧
-- **网络不通的三种解法**：一是用 `Watt Toolkit` 加速软件，进入网站选对应版本下载安装，打开后勾选「GitHub 加速」即可流畅访问；二是用 GitHub 镜像站（如 `gh-proxy`），浏览器直接打开即可，但速度和稳定性较差；三是用「魔法」（VPN），注册 GitHub 用国内 QQ 邮箱即可。
-- **页面汉化**：给浏览器装翻译插件，谷歌浏览器推荐 `Google Translate` 或沉浸式翻译，安装后可将网页翻译成中文；动手能力强的可安装汉化插件。
-- **原生搜索的局限**：GitHub 原生搜索按搜索词精准匹配，如搜 `screen record` 和 `screen recording` 结果不同，对国人不好用。
-- **AI 搜索替代方案**：用 ChatGPT 等 AI 工具以中文描述需求（如「在 GitHub 上帮我找好用的录屏软件」），可搜齐热门工具并总结成表格，弥补英文不好与精准匹配的不足。
-## 项目主页结构与维护判断
-- **项目主页构成**：项目本质是文件夹，`watch` 是关注、`fork` 是复制到自己的账号、`star` 是收藏点赞；`about` 是项目简介，`release` 是软件安装包，`readme` 是项目说明书，默认在项目最下方展开显示。
-- **僵尸项目判断**：查看文件最近的 `commit` 日期（即最近更新时间），若更新日期是好几年前，大概率是没人维护的僵尸项目。
-- **热门项目追踪**：点开左侧 `explore` 的 `trending`，可查看全站当天、本周、本月最热门项目；也可让 ChatGPT 帮忙找 GitHub 每日热门项目。
+## 工作性价比评估
+- 输入**年薪**、工作地区、年假、通勤时长、学历、工作年限、领导同事等因素，综合输出工作性价比分数与评级。
+- 老李测试此前程序员工作，评估结果为「性价比还不错，优质牛马」。
+## 表情包博物馆
+- 收集国内过去几年全网爆火的表情包大合集，涵盖甄嬛传、罗翔、特朗普、马保国等主题，用于斗图可「把对方按在地上摩擦」。
+## 健康活到150岁指南
+- 分享经科学验证的健康知识，如**间歇性进食**促进胆汁代谢、炎症自愈，吃天然发酵类食品可改善肠道菌群生态。
+## 一键做证件照
+- 上传一张大头照即可一键抠图换背景，生成不同标准的证件照及各种规格的打印模板。
+## 丐版健身教练
+- 选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，适合请不起真人教练的用户。
+## 教材资源项目
+- 收集国内所有小学、初中、高中及部分大学的PDF教材，全部免费使用。
+## 全自动视频生成项目
+- 名为 `Morning Printer Turbo`，为近期热门的全自动视频生成工具。
+## 声音克隆模型 ChatTTS
+- **零样本语音克隆**模型，情感控制到位，克隆声音接近真人；上传一段自己的音频即可合成指定台词。
+## AI学习资源库
+- 涵盖大语言模型、`RAG`、`AI Agents` 等最新AI技术，作者整理成**500多页PDF文档**，含大量示意图辅助理解。
+## Awesome AI Apps
+- 收录大模型最新的 `agent` 应用，如医学影像数据分析、AI投资、竞争对手情报分析等，可用于跟进AI应用落地案例或寻找创业点子。
+## GitHub访问加速
+- 方法一：使用 `Watt Toolkit` 加速软件，进入官网选择对应电脑版本下载安装，打开后找到网络加速勾选 `GitHub加速` 即可流畅访问。
+- 方法二：使用GitHub镜像站（如 `gh-proxy`），浏览器直接打开即可访问，可搜索GitHub其他项目，但速度与稳定性较差。
+- 方法三：使用魔法（VPN），老李个人最推荐此方法。
+## GitHub注册与汉化
+- 注册简单，用国内QQ邮箱即可完成。
+- 汉化可给浏览器安装翻译插件，谷歌浏览器推荐 `Google Translate` 或 `沉浸式翻译`，安装后可直接将网页翻译成中文；动手能力强的可安装汉化插件。
+## GitHub搜索技巧
+- 顶部搜索框按关键词搜索项目，默认按匹配度排序，更常用的是按 `star数` 排序，star越多代表项目越受欢迎。
+- 原生搜索按精准匹配，如搜 `screen record` 与 `screen recording` 结果不同，对国人不够友好。
+- 推荐用AI搜索，如在ChatGPT中用中文描述需求，可自动找齐热门项目并总结成表格。
+## 项目主页功能
+- GitHub项目本质是一个文件夹，`watch` 是关注项目，`fork` 是复制项目到自己的账号，`star` 相当于收藏和点赞。
+- `About` 为项目简介，`release` 为软件安装包，`readme` 是项目说明书，默认在项目最下方展开显示。
+- 每个文件的最近 `commit` 日期即最近更新时间，若更新日期久远，大概率是无人维护的僵尸项目。
+- 通过左侧 `Explore` 进入 `Trending`，可查看全站当天、本周、本月最热门项目；也可用ChatGPT找 `GitHub daily` 获取最新热门项目。
 # 核心结论
 ## 核心结论
-- **GitHub定位**：GitHub不仅是代码托管平台，更是巨大的宝藏资源库，几乎想找的资源、教程、工具都能找到，包括名校公开课、大厂面试题、开源大模型、AI学习资料等。
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事是否SB等因素，综合给出工作性价比分数和评级；老李测试程序员工作，评估结果为「性价比还不错，优质牛马」。
-- **表情包博物馆**：收录国内过去这些年全网爆火的表情包大合集，包括甄嬛传、罗翔老师、特朗普、马保国等，可用于斗图。
-- **健康指南项目**：分享经科学研究证实的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态，目标是「活到150岁」。
-- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准的证件照和各种规格的打印模板。
-- **自重健身教程**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，适合请不起真人教练的用户。
-- **教材资源项目**：收集国内所有小学、初中、高中及部分大学的PDF教材，全部免费使用。
-- **全自动视频生成项目**：Morning Printer Turbo，近期超火。
-- **声音克隆模型ChatBox TTS**：零样本语言克隆，情感控制到位，克隆声音像真人说话；上传一段音频即可合成英文台词。
-- **AI学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术，作者整理成500多页PDF文档，含大量示意图。
-- **Awesome AI Apps项目**：收录大模型最新的Agent应用，如医学影像数据分析、AI投资、竞争对手情报分析等，适合跟进AI应用落地案例或寻找创业点子。
-- **访问GitHub的三种方法**：Watt Toolkit加速软件（更流畅）、GitHub镜像站gh-proxy（速度与稳定性较差）、VPN魔法（个人最推荐）。
-- **GitHub注册**：注册很简单，用国内QQ邮箱即可。
-- **页面汉化**：给浏览器装翻译插件即可，谷歌浏览器推荐Google Translate或沉浸式翻译，安装后可直接将网页翻译成中文；动手能力强的可安装汉化插件。
-- **AI搜索替代原生搜索**：GitHub原生搜索按搜索词精准匹配，如搜screen record和screen recording结果不同；推荐用ChatGPT等AI工具用中文描述需求，可找到热门工具并总结成表格。
-- **项目主页构成**：项目本质是文件夹，watch是关注、fork是复制、star是收藏点赞，about是项目简介，release是软件安装包，readme是项目说明书。
-- **判断僵尸项目**：查看文件最近的commit日期，若更新日期是好几年前，大概率是没人维护的僵尸项目。
-- **查看热门项目**：点开左侧explore的trending，可看到全站当天、本周、本月最热门的项目；也可让ChatGPT帮忙找GitHub daily，及时分享最新最热门项目。
+- **GitHub 是综合性资源库**：可找到名校公开课（麻省理工、斯坦福）、大厂面试题与经验（字节、阿里、腾讯）、开源大模型（Google、阿里）、AI 副业教程及表情包合集、养生指南、大厂黑名单等资源。
+- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事等因素，输出性价比分数和评级；老李测试程序员工作，结果为「性价比还不错，优质牛马」。
+- **表情包博物馆项目**：收录国内过去几年全网爆火的表情包合集，含甄嬛传、罗翔、特朗普、马保国等主题。
+- **健康活到 150 岁指南**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态。
+- **一键做证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照和各类规格打印模板。
+- **丐版健身教练项目**：选择要练习的肌肉群（如腹肌），提供身体自重练习的参考动画，适合请不起真人教练的用户。
+- **教材资源项目**：收集国内小学、初中、高中及部分大学的 PDF 教材，全部免费使用。
+- **全自动视频生成项目**：Morning Printer Turbo，近期热门。
+- **ChatBox TTS 声音克隆模型**：零样本语音克隆，情感控制到位，克隆声音接近真人；上传音频即可合成指定英文台词。
+- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
+- **Awesome AI Apps 项目**：收录大模型最新 agent 应用，如医学影像数据分析、AI 投资、竞争对手情报分析等，可跟进 AI 应用落地案例或寻找创业点子。
+- **国内访问 GitHub 三种方法**：Watt Toolkit 加速软件（官网下载安装后勾选 GitHub 加速）、镜像站（如 gh-proxy，浏览器直接打开即可，但速度与稳定性较差）、魔法（VPN）；老李个人最推荐第三种。
+- **GitHub 注册与汉化**：注册可用国内 QQ 邮箱；汉化可装浏览器翻译插件，谷歌浏览器推荐 Google Translate 或沉浸式翻译，动手能力强的可装汉化插件。
+- **GitHub 搜索技巧**：原生搜索按精准匹配排序，搜「screen record」与「screen recording」结果不同；推荐用 ChatGPT 等 AI 工具以中文描述需求，可汇总热门项目并总结成表格。
+- **项目主页功能**：watch 为关注、fork 为复制到自己的账号、star 为收藏点赞；About 为项目简介，release 为安装包，readme 为项目说明书，文件最近 commit 日期可判断项目是否有人维护。
+- **发现热门项目**：通过 Explore→Trending 查看全站当天、本周、本月最热门项目；也可让 ChatGPT 找 GitHub daily 获取最新热门项目。
 ## 易混点与适用边界
-- **Watt Toolkit vs 镜像站**：Watt Toolkit加速软件更流畅，镜像站（gh-proxy）速度和稳定性更差；但个人最推荐的是VPN魔法。
-- **GitHub原生搜索的局限**：按搜索词精准匹配，同一含义的不同英文表达（如screen record和screen recording）搜出的结果不同，对英文不好的用户不友好。
-- **镜像站使用范围**：gh-proxy默认是镜像的项目地址，但搜索GitHub其他项目没有任何问题。
-- **翻译插件适用场景**：谷歌浏览器推荐Google Translate或沉浸式翻译，翻译效果基本够用；汉化插件适合动手能力强的用户。
-- **star数的含义**：项目star数即其「江湖地位」，star越多说明项目越受欢迎，排序时更常用按star数排序而非默认的匹配度排序。</t>
+- **Watt Toolkit 与镜像站对比**：Watt Toolkit 更流畅，镜像站速度和稳定性更差；镜像站默认打开的是镜像项目地址，但搜索其他项目不受影响。
+- **GitHub 原生搜索与 AI 搜索对比**：原生搜索按关键词精准匹配，同一含义的不同写法（如 screen record 与 screen recording）结果不同；AI 搜索可弥补英文不好、搜不准不全的问题。
+- **star 与 watch、fork 的区别**：star 相当于收藏点赞，代表项目受欢迎程度（江湖地位）；watch 是关注项目动态，fork 是复制项目到自己的账号。
+- **readme 与 About 的区别**：About 是一句话项目简介，readme 是详细说明书，默认在项目最下方展开显示，是了解项目必看内容。
+- **commit 日期判断项目状态**：文件最近 commit 日期即最近更新时间，若更新日期是好几年前，大概率是没人维护的僵尸项目。</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>40.9</v>
+        <v>42.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4014/3765</t>
+          <t>4014/3531</t>
         </is>
       </c>
     </row>
@@ -5400,83 +5298,83 @@
       <c r="C16" t="inlineStr">
         <is>
           <t># 访谈概述
-本期《锵锵三人行》由主持人邀请《明朝那些事儿》作者当年明月，以及嘉宾马先生、发言者3、发言者4，围绕刚播完的日本历史剧《大奥》展开对谈，并延伸至明朝历史与文化。节目先探讨《大奥》所反映的日本文化精神，再转入明史魅力、朱元璋评价、明朝兴亡经验及明式家具等话题。
-关于《大奥》，发言者3认为它是继《大长今》后最有影响的国外电视剧，当年明月认同并指出其吸引人之处在于严谨的精神。讨论涉及《大奥》的历史背景（前两部对应中国晚明到清初，第三部在明治维新前）、大奥即后宫的含义、日本天皇与幕府将军的权力关系（天皇为摆设，德川家康后权力集中于幕府将军）、日本文化的极端精神（所有事情做到尽头）、战后日本用30年成为世界第二经济强国（以绝对量计，是强国中唯一没有资源的国家）、中日文化差异（中国中庸、日本坚持一个原则）、日本人的低跳槽率与终身雇佣制下的高积极性等。
-关于明朝历史，当年明月解释自己写明朝是因为明史资料最多，历史研究难点在先秦（没史料）和明清（说法太多）。发言者3补充明朝260多年过程跌宕起伏，如土木堡之变、夺门之变。当年明月推崇朱元璋，因其从乞丐到皇帝独此一份，且明朝规章制度由他定下基本无大改动。讨论还涉及英雄史观、历史经验教训（从历史中得到的唯一教训就是我们从来没有从历史中得到过教训）、明末市民生活轻松舒服、江浙工商业兴起、李自成起义因陕西灾荒、明末工艺精细、文征明唐寅董其昌等人物、明代宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣）等。
-节目还讨论了明式家具的国际地位，发言者3认为明式家具地位高绝非偶然，与当时社会时尚和皇帝（如天启帝爱当木匠）的推动有关。关于明朝皇帝的评价，当年明月指出正德皇帝（明武宗）被写坏，因明武宗实录由嘉靖指派杨廷和等人编纂，存在偏颇。
+本期《锵锵三人行》由主持人感谢马先生携《明朝那些事》作者当年明月做客，围绕刚播完的日本历史剧《大奥》展开讨论，并延伸至明朝历史与文化。马先生认为《大奥》是继《大长今》后最有影响的国外电视剧，当年明月亦表认同。三人就《大奥》的历史背景、日本礼仪、大奥含义、幕府将军与天皇关系，以及日本人的极端精神、忠诚文化、终身雇佣制等话题进行了交流。
+关于日本文化，马先生指出日本战后1945年用30年成为世界第二经济强国，以绝对量计是强国中唯一没有资源的国家；日本人的跳槽率最低，终身雇佣制下积极性仍高。当年明月认为日本文化从头到尾没有变，体现为极端精神，所有事情要做到尽头，并对比中日文化差异，称中国文化精神是中庸，日本精神则坚持一个原则。马先生以豆腐厂当天做当天卖、夜里11:45坐好、12点整开始工作、四点多干完上市为例，说明日本人的一丝不苟。
+关于明朝历史，当年明月解释写《明朝那些事》是因为明史资料最多，但史料矛盾多，一个事件可能有7个不同说法。马先生补充明朝260多年过程跌宕起伏，多次差点灭亡，如土木堡之变、夺门之变。三人讨论朱元璋从乞丐当上皇帝独此一份，定下明朝规章制度基本没有太大改动；明末市民生活轻松舒服，江浙工商业兴起，出现三言二拍等娱乐产品；李自成起义因陕西大规模灾荒；明末工艺变得精细，日本派大量工匠学习。当年明月总结历史经验教训：我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
+关于审美差异，马先生认为宋明是典型的汉人政权，文人欣赏审美较高，对美的判断不是表象的；满族进来后对美的判断都是表象的，所以故宫金碧辉煌的大红大紫是满族趣味。当年明月补充明代皇帝有趣，如明武宗正德要去江南被大臣跪谏阻止，明神宗几十年不上朝，天启皇帝爱当木匠。马先生还提到正德皇帝被嘉靖时期编的实录写坏，因其非嘉靖亲生，嘉靖指派杨廷和等人编纂，存在偏颇。
 # 访谈详细记录
 ## 日本历史剧《大奥》与日本文化
-- **《大奥》播出反响**：发言者3认为《大奥》是继《大长今》以后最有影响的国外电视剧，当年明月表示认同，认为确实是一部拍得非常好的作品。
-- **《大奥》历史背景**：发言者3指出该剧三部，前两部相当于中国晚明到清初时段；当年明月补充第三部在明治维新之前，是一部有跨越性的历史剧。
-- **当年明月观剧感受**：当年明月表示是晚上没事临时翻到的，吸引他的是剧中「严谨的精神」——回头看《三国演义》会看到群众演员笑，但日本剧看不到笑。
-- **《大奥》礼仪场面**：发言者3描述第一集片头将军出场时所有人呈45度鞠躬、依次鞠躬，场面华丽色彩讲究，「一看就不一样」。
-- **大奥词义解释**：发言者3解释大奥即中文的「后宫」，日语「奥」指很深的地方、屋子最里处；发言者1补充中文保留「堂奥」「深奥」等痕迹；当年明月补充另一含义是一般人不准进去。
-- **日本权力结构**：当年明月陈述天皇一直是摆设，实际权力在幕府将军手中；德川家康开创德川幕府后，日本所有权力掌握在一个人手上。
-- **天皇受制于幕府**：当年明月举例，德川家掌权后天皇想举办活动但没钱，找将军要钱被拒，活动未办成，天皇后来以退位抗议幕府。
-- **中日权力结构差异**：当年明月对比明朝皇帝不上朝与日本天皇无权——明朝大臣仍听皇帝的、不敢造反，而日本天皇实际没有权力；发言者3补充日本从唐朝开始一直是军人政权。
-- **日本极端精神**：当年明月认为从《大奥》可看出日本文化从头到尾没变，体现为「极端精神」——所有事情要做到尽头；发言者3认为这是发自内心的，与中国人不同。
-- **战后日本经济成就**：发言者3陈述日本1945年战后用30年成为世界第二经济强国（以绝对量计），是强国中唯一没有资源的国家。
-- **中日文化精神对比**：当年明月以马先生家具店所见硬木刻云彩为例，说明中国精神是「中庸」——不是对错黑白之间，而是最适合的路；日本精神恰相反，坚持一个原则，如炮手开炮时忘记一切只记得把炮开出去即达最高境界。
-- **日本忠诚文化**：发言者3认为日本是忠诚文化的典型国度，坚韧不拔、做事做到极致；发言者1提及有批评称日本人的忠诚是「家奴」。
-- **日本低跳槽率**：发言者3指出日本跳槽率最低，每次跳槽都是社会资源浪费；当年明月补充西方经济学家不能理解日本终身雇佣制下缺乏竞争却积极性高，是「经济学上的奇迹」。
-- **《大奥》忠诚情节**：发言者1复述剧中情节——女子入大奥前有情人发誓救她，将军死后情人放火来救，女子却拒绝跟走并质问对方是否想到大奥里有1000个女人，后落发出家。
-- **阿福的忠诚典范**：发言者3陈述《大奥》第一集阿福25岁进大奥当奶妈、65岁去世，40年做事完全出于公心、不夹杂私利，被伤害的人也认为他出于公心，最终被所有人视为楷模。
-- **角色分工与效率**：当年明月引述「慢慢来才是最快的方法」，认为所有人按自己角色做事最节省成本、不互相抵消，形成合力非常可怕。
-- **日本豆腐厂见闻**：发言者3描述参观日本最底层工厂——豆腐厂规定当天做当天卖，工人夜里11:45坐好不动看表，12点整准时起立开工，四点多干完上市，期间无人闲聊。
-- **岛国生存环境与团体规则**：当年明月认为日本是岛国、没有资源、常火山地震，人跑都没地方跑，有极强求生欲望，对世界悲观，必须融入团体按固定规则做事才能生存。
-- **投机取巧者无生存环境**：发言者3认为日本投机取巧的人没有生存环境，社会文化鄙视使其难以生存。
-- **日本商人案例**：发言者3举例日本做绳子做到全日本第一的人，几年内批发转送一分钱不赚，铺平市场后向两边各要2%，靠4%差价赚大钱。
-- **是否愿做日本人**：发言者3表示在中国文化中「愿意也做不成」，文化不允许这种现象生存；当年明月表示不愿意，因日本人很多时候盲从，且有「寻死的潜在欲望」。
-- **日本人的死亡观**：当年明月认为日本人看樱花只看落的那一天，因岛国生存条件恶劣，对死亡不惧怕甚至有点向往；发言者3纠正为「不是藐视生命，是重视死亡」，并举经济危机时身家万贯者剖腹自杀为例。
+- **《大奥》播出反响**：马先生认为《大奥》刚播完引起很大反响，是《大长今》以后最有影响的国外电视剧；当年明月表示认同，认为确实是一部拍得非常好的剧。
+- **《大奥》历史背景**：马先生介绍该剧共三部，前两部相当于中国晚明到清初时段，后一部在明治维新之前，是一部有跨越性的历史剧。
+- **大奥的含义**：马先生解释大奥即普通话所说的后宫，日语中"奥"指很深的地方、屋子最里处；当年明月补充另一层意思是一般人不准进去。
+- **大奥的规模**：马先生指出幕府将军与1000个女人生活在大奥，这1000个女人全是伺候将军一个人的，是一种生活方式。
+- **天皇与幕府关系**：当年明月介绍日本天皇一直是摆设，实际权力在幕府将军；德川家康开创德川幕府后，日本所有权力掌握在一人手上。
+- **天皇受制于幕府**：当年明月举例，天皇曾想举办活动但没钱，找将军要钱被拒，活动未办成，天皇后来以退位表示对幕府抗议。
+- **中日皇权差异**：当年明月对比明朝皇帝不上朝与日本天皇无权，认为明朝大臣仍听皇帝的、不敢造反，而日本天皇实际没有权力。
+- **日本军人政权传统**：马先生指出日本很长一段时间都是军人政权，相当于从唐朝开始一直是军人坐第一把交椅。
+- **日本极端精神**：当年明月认为从《大奥》可看出日本文化从头到尾没有变，体现为一种极端精神，特点就是所有事情要做到尽头。
+- **日本战后经济成就**：马先生认为日本1945年战后用30年成为世界第二经济强国（以绝对量计），不是偶然而是必然，源于全民族的极端精神；日本是强国中唯一没有资源的国家。
+- **终身雇佣制**：当年明月提到日本跳槽率最低，西方经济学家不理解日本终身雇佣制缺乏竞争却仍保持高效率，这是经济学上的一个奇迹。
+- **阿福的忠诚**：马先生介绍《大奥》第1集阿福25岁进大奥当奶妈，65岁去世，40年无论做什么事完全出于公心、不夹杂私利，所有人最终都认为她是楷模。
+- **忠诚文化的体现**：马先生认为阿福的故事是日本忠诚文化的具体体现，不是靠说教而是靠具体事例；剧中女人放弃爱情、落发出家也是忠诚文化的表现。
+- **各司其职的效率**：当年明月认为日本文化思维方式是做事不夹杂自己的想法，所有人按自己角色做事最节省成本，形成合力非常可怕。
+- **豆腐厂案例**：马先生讲述参观日本最底层豆腐厂，规定当天做当天卖，夜里11:45所有人坐好不动，12点整准时开始工作，四点多干完上市，无人闲聊。
+- **岛国生存压力**：当年明月认为日本作为岛国没有资源、常火山地震，人本身有极强求生欲望，对世界悲观，必须融入团体按固定规则做事才能生存。
+- **投机取巧无生存环境**：马先生认为日本投机取巧的人没有生存环境，社会文化的鄙视非常难过；举例日本做绳子做到全日本第一的人，几年不赚钱铺市场，最后靠4%的差价赚大钱。
+- **日本人的死亡观**：当年明月认为日本人因生存条件恶劣，对死亡不是藐视而是有点向往、不惧怕，看樱花只看落的那一天；马先生认为日本民族不是藐视生命而是重视死亡，经济危机时很多身家万贯的人剖腹自杀。
+- **二战暴行的解释**：当年明月认为二战时日军在中国的暴行是一种藐视生命的行为。
 ## 明朝历史与《明朝那些事》
-- **《明朝那些事》热销**：发言者3指出该书发行量在排行榜第一，各报文学类都是第一；发言者1评价「写得好、写得放松」，认为作者喜欢自己写的东西，有调侃开玩笑的挥洒感。
-- **写作风格原因**：当年明月表示「不知道什么拘着，我就只能这么写」；发言者3对比过去写史书的人「都拘着，生怕哪块做的不合适」，而广大读者了解历史「大概是怎么回事就行了」。
-- **为何写明朝**：当年明月表示最诚实的原因是「明史是我最熟」，因明史资料最多；历史研究有两个难点——先秦春秋没史料（如孙武事迹在《史记》仅一两篇，都是编的），明清说法太多。
-- **明史史料矛盾**：当年明月举例明实录几千万字，加上明通鉴、明史纪事本末、明会典、纲目三编等堆得比山还高，但一个事件可能有7个不同说法，如同黑泽明电影《罗生门》。
-- **明朝过程跌宕起伏**：发言者3认为明朝260多年过程本身跌宕起伏，几次要死没死了，如土木堡之变、夺门之变——皇上被瓦剌军抓了，哥几个把弟弟扶起来，「完全构成一个现代版的电视剧」。
-- **推崇朱元璋的原因**：当年明月认为朱元璋从乞丐到当上皇帝太不容易，且明朝规章制度由他定下、基本无大改动，「是多了不起的人才」；发言者3补充历史上最底层的人坐到最上面「独此一份」。
-- **英雄史观**：发言者3认为「人的因素最大，改变时势一定是出现一个人」；发言者1评价这是英雄史观，有常人不及的地方。
-- **朱元璋的天分**：当年明月以《亮剑》李云龙类比——没上过军事院校但会打仗，是战场上积累经验形成的天赋；朱元璋天分相当高。
-- **朱元璋参加起义是被逼**：当年明月陈述朱元璋原在庙里犹豫不去，因汤和来信被信差听到、被人告发，没办法只能去起义；他强调历史最重要的是弄明白「它是发生过的」，旁观者觉得好玩，但当年造反是要掉脑袋的风险。
-- **历史认知的局限**：发言者3认为站在历史原点时前后都看不见，必须撤出来才能看见；发言者4补充「你当时都不聪明」。
-- **明朝经验体现**：发言者3认为明朝有仁宣盛世等不错时期，晚明政治虽黑暗、皇帝不上朝，但老百姓生活很好；发言者4以《金瓶梅》中西门庆为例，说明那是明代市民生活的一个阶层。
-- **明末市民生活**：当年明月陈述明末市民生活轻松舒服、想去哪去哪，皇册都不用，江浙一带工商业兴起、给人当雇工活得很滋润；三言二拍等娱乐产品出现说明有养活自己的资本。
-- **李自成起义原因**：当年明月指出李自成起义是因为陕西一带发生大规模灾荒。
-- **明末工艺与艺术**：发言者3认为明末工艺彻底改观、变得精细，日本派大量工匠来中国交流；文征明、唐寅、董其昌都是那个时期的人，生活好才画得出小桥流水；到八大山人时画翻白眼，是对社会愤愤不平。
-- **历史教训**：当年明月提出「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因为历史发生时有背景，你不比前人聪明，甚至可能比前人笨；史书只是「照片」，古人的生活是「录像」，不知道那一幕之前和之后是什么，所以千万不能套用。
-- **明代有趣之处**：当年明月列举明代宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣），「谁都可能当老大」；皇帝出去了还能回来做皇帝。
-- **吴三桂入关原因**：当年明月陈述吴三桂与满清合作入关，除陈圆圆外还因崇祯皇帝死了——当时说法是「入关为崇祯皇帝复仇」，吴三桂很忠诚于崇祯。
-- **1644年北京瘟疫**：当年明月提及1644年李自成军打到京城无人抵抗，因有些史料记载当时北京闹瘟疫「疙瘩瘟」（即天花）；他曾与老师王佩奇先生交流，认为明朝亡得蹊跷，「什么坏事衰事赶上了」。
-- **王朝300年大限**：发言者3认为中国历史王朝逼近300年就完了，如同人活到八九十岁大限快到；严格讲跨过300年的只有宋朝（南北宋接上，退让大半个国土延续319年），汉朝中间隔断14年，唐朝明朝清朝都没跨过。
-- **明朝如大公司**：当年明月以公司类比——世界超过276年的公司没几家，明朝是几千万人的大摊子，能撑276年已属不易。
-## 明式家具与明朝皇帝评价
-- **明清审美差异**：发言者1提出一种观点——故宫金碧辉煌的大红大紫是满族趣味，真正明朝不是这样；发言者3认为宋明是文人政权、审美高、对美的判断不是表象，满族是异族、对美的判断是表象的；晚清到民国初年收藏中素雅的东西才值钱，今天外在直观美的东西卖得贵。
-- **明武宗下江南受阻**：当年明月陈述正德皇帝要去江南，大臣全跪金水桥前抗议，皇帝气坏了到锦衣卫打死了十几个人，还是不让去。
-- **史官冒死求名**：发言者1提及明朝有史官故意对皇帝说难听话、求砍头以青史留名的现象；发言者3认为这是文化的力量，「超出我们想象的力量」。
-- **明武宗扬州打秋风**：当年明月陈述正德皇帝到扬州要东西被拒，不生气，让人准备酒席后说吃不了，要求把酒席折合成银两带回去。
-- **天启帝当木匠**：发言者3陈述天启帝干完木工活差大臣去卖，还打听卖得怎么样，卖得很好就成就感特大；发言者4调侃「你要是再亲自去卖，那还好卖呢」。
-- **明式家具地位**：发言者3认为天启帝当木匠从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然，「所有的偶然中一定有个必然的因素」。
-- **正德皇帝被写坏**：当年明月认为正德皇帝被写坏是因为接班的嘉靖不是他亲生、是堂兄弟，嘉靖指派杨廷和等人编明武宗实录，有偏颇；豹房其实有动物园、养了豹子，女人在后宫也有，「放哪都是一样的」。
-- **正德皇帝有城府**：当年明月举例正德从江南回来先在通州停半天，先派人打探京城有没有埋伏圈套，说明「这个人绝不是史料上所写的那么蠢」。
-- **嘉靖大礼仪事件**：当年明月提及嘉靖上台搞大礼仪事件，为给自己父亲（王爷）追封皇帝争名分，为此死了很多人、折腾了很多人。
-- **正德皇帝无后**：发言者3指出正德是明朝定论最荒淫的皇帝，没少找女人但不留种、没有生育能力；对宫廷外女人有兴趣，因宫廷内女人禁忌太多、太保守。
-- **历史研究的傲慢与偏见**：发言者1批评很多专家研究历史有「傲慢与偏见」，没有设身处地，老觉得自己聪明、判断前人昏庸无能。
+- **《明朝那些事》热销**：马先生介绍该书发行量在排行榜第一，各报文学类都是第一；主持人评价写得好看、放松，调侃挥洒有意思。
+- **写作风格原因**：当年明月回应自己不知道什么叫"拘着"，只能这么写；马先生认为过去写历史书的人都拘着，怕哪块做得不合适，其实对广大读者来说大概是怎么回事就行了。
+- **写明史的原因**：当年明月表示明史资料最多，历史界研究有两个难点：先秦春秋没史料，明清史料太多但矛盾多，一个事件可能有7个不同说法，如同黑泽明电影《罗生门》。
+- **明朝历史跌宕起伏**：马先生认为明朝260多年过程本身就跌宕起伏，几次要死没死，如土木堡之变、夺门之变，皇上被瓦剌军抓起来又扶弟弟上位，构成现代版电视剧情节。
+- **推崇朱元璋的原因**：当年明月认为朱元璋从乞丐当上皇帝，历史独此一份；刘邦好歹是村长或乡长，朱元璋要过饭，知道每一层的猫腻，疑心重，但此人太不容易。
+- **朱元璋的制度贡献**：当年明月指出明朝规章制度由朱元璋定下来，基本上没有太大改动，认为他是了不起的人才。
+- **英雄史观**：马先生认为人的因素最大，改变时势一定是出现一个人；当年明月认为朱元璋天分相当高，如同《亮剑》中李云龙没上过军事院校却能打仗，是战场上积累经验的天赋。
+- **朱元璋参加起义的经过**：当年明月讲述朱元璋原在庙里犹豫不去参加起义军，因信差送信被听到告发，没办法只能去起义；强调历史最重要的是弄明白这事是真的，当年造反是要掉脑袋的风险。
+- **历史认知的局限**：马先生认为回头看历史谁都是聪明人，但站在历史原点时前后都看不见，必须撤出来才能看见；当年明月补充历史事件发生时有背景，你不比前人聪明，甚至可能比前人笨。
+- **明末市民生活**：当年明月指出明末很多真相被掩盖，市民生活特别轻松舒服，想去哪去哪，皇册都不用了；江浙一带兴起工商业，给人当雇工活得很滋润，出现三言二拍这类娱乐产品说明有养活自己的资本。
+- **李自成起义原因**：当年明月解释李自成起义是因为陕西一带发生大规模灾荒。
+- **明末工艺与艺术**：马先生指出明末工艺变得非常精细，有点像日本工艺，日本派大量工匠来中国交流；文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水，八大山人画翻白眼是对社会愤愤不平。
+- **历史教训**：当年明月总结"我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训"，认为史书记载的只是照片，而古人的生活是录像，不知道前因后果，不能套用经验否则一定倒霉。
+- **明代朝代的趣味性**：当年明月认为明代有趣在什么事都有：宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣），谁都可能当老大。
+- **吴三桂入关原因**：当年明月提到吴三桂与满清合作入关，除陈圆圆外还有一个原因是认为崇祯死了，说法是入关为崇祯皇帝复仇。
+- **1644年北京瘟疫**：当年明月提到有史料记载1644年明朝灭亡那年北京闹瘟疫，叫疙瘩瘟，即天花；他曾与老师王佩奇交流，认为明朝亡得蹊跷，什么坏事衰事都赶上了。
+- **王朝300年大限**：马先生认为中国历史王朝约300年是大限，逼近300年就完了；严格讲跨过300年的只有宋朝（南北宋接上，退让大半个国土延续319年），汉朝中间隔断14年，唐朝明朝清朝都没跨过。
+- **明朝如公司**：当年明月比喻明朝像一家几千万人的大公司，超过276年的公司没几家；毛老师安慰他，一公司成立200多年够本了。
+## 审美差异与明代皇帝
+- **明清审美差异**：马先生认为宋明是典型汉人政权、文人政权，文人欣赏审美较高，对美的判断不是表象的；满族进来后对美的判断都是表象的，故宫金碧辉煌的大红大紫是满族趣味。
+- **收藏审美的变迁**：马先生指出晚清到民国初年的收藏中，外在美直观能看到的都不值钱，一定是素雅的；今天凡是外在美直观能看到美的都卖得非常贵。
+- **明武宗被阻出行**：当年明月讲述明武宗正德要去江南，大臣跪在金水桥前抗议不让去，皇帝气坏了到锦衣卫打死了十几个人，还是不让去。
+- **正德皇帝打秋风**：当年明月举例正德皇帝到扬州要东西，政府说没有；皇帝不生气，让人准备酒席，吃不了就折合成银两带回去。
+- **天启皇帝当木匠**：马先生介绍天启皇帝爱当木匠，干完活差大臣去卖，回来还打听卖得怎么样，卖得很好就成就感特大；认为这从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然。
+- **正德皇帝被写坏**：当年明月认为正德皇帝被嘉靖时期编的《明武宗实录》写坏，因嘉靖不是正德亲生而是堂兄弟，接班的嘉靖不能把他写得太好；豹房其实有动物园养豹子，不是史料所写的那么荒淫。
+- **正德皇帝有城府**：当年明月举例正德从江南回来先在通州停半天，派人打探京城有没有埋伏圈套，认为此人绝不是史料所写的那么蠢。
+- **嘉靖大礼仪事件**：当年明月提到嘉靖上台搞大礼仪事件，为给自己父亲争名分（追封为皇帝）死了很多人、折腾了很多人。
+- **正德皇帝无后**：马先生指出正德是明朝最荒淫的皇帝，没少找女人但不留种，没有生育能力；清朝最荒淫的是咸丰，但咸丰还留了个种。
+- **正德对宫外女人有兴趣**：马先生认为正德对宫廷内女人没兴趣，因禁忌太多、太保守；对宫廷外女人有兴趣，因民女不知他是谁。
+- **史官冒死进谏**：主持人提到明朝有些史官把冒死进谏当时尚，就是要跟皇帝说难听的让皇帝砍头，为青史留名；马先生认为这是文化的力量，超出我们的想象。
 # 关键引语与金句
-&gt; 慢慢来才是最快的方法。所有人按照自己的角色去做自己的事情，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。
-&gt; 中国的文化精神是什么？是中庸。……不是对，也不是错，不是黑也不是白，不是真理，也不是谬误，你就是太极。但是这条路可以走得通叫融合。
-&gt; 日本的精神就恰相反，他坚持一个原则，你看鞠一刀就知道，所以说比方说一个炮手在开炮的时候，当他忘记所有的事情，只记得把这一炮开出去，它就达到了它的最高境界。
+&gt; 慢慢来才是最快的方法。
+背景：当年明月回应主持人关于日本文化中「不偷奸耍滑」的讨论，说明按角色做事、不夹杂小聪明反而最有效率。
 &gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-&gt; 历史它那个事儿发生的时候是有背景的……史书上记载下来是什么。照片，我打个比方是照片照片，而我们实际上我们的生活，古人的生活都是录像。
-&gt; 日本的文化跟中国的文化存在一个极大的不同。……资源是0。
-&gt; 明朝无论怎么样，大臣还是听皇帝的，他也不敢造皇帝的反，但是实际上在日本的天皇是没有权力的。</t>
+背景：当年明月回应主持人关于明朝经验教训能否体现于兴亡的提问，指出历史事件有其背景，不能简单套用经验。
+&gt; 日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是什么？是中庸。
+背景：当年明月对比中日文化差异时提出，以马先生家具店中「硬木刻云彩」为例说明中国讲究融合与最适合之路。
+&gt; 日本战后1945年用30年的时间成为世界第二经济强国，它不是一个偶然，它是一个必然。
+背景：马先生回应日本极端精神的讨论，以战后经济崛起说明全民族极端精神的作用，强调日本是强国中唯一没有资源的国家。
+&gt; 明朝无论怎么样，大臣还是听皇帝的，他也不敢造皇帝的反，但是实际上在日本的天皇是没有权力的。
+背景：当年明月回应主持人关于幕府将军是否崇拜天皇的提问，对比中日皇权与臣属关系的差异。
+&gt; 历史它那个事儿发生的时候是有背景的……你不比前人聪明，你甚至可能比前人笨，当那种情况出现的时候，你也得那么办。
+背景：当年明月回应主持人关于历史经验总结的讨论，说明史书只是「照片」而古人的生活是「录像」，不能脱离背景评判前人。</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>95.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14719/5506</t>
+          <t>14719/5035</t>
         </is>
       </c>
     </row>
@@ -5813,38 +5711,39 @@
       <c r="C17" t="inlineStr">
         <is>
           <t># 就诊概况
-患者严某，男，48岁，在成都轻工研究所从事科研工作。就诊于消化专科，接诊医生为张学恒。本次就诊核心主诉为上腹反复疼痛4年、近3个月加重，伴两次黑便及呕吐。医生初步了解病情后，安排留大便检查及胃镜，胃镜预约在后天进行。
+本次门诊由消化专科医生严医生接诊48岁男性患者张学恒，患者为成都轻工研究所科研人员。就诊围绕上腹反复疼痛4年、近3月加重的主诉展开，疼痛位于心窝处，有烧灼感，进食冷、硬、刺激性食物或工作紧张时发作，近3个月出现两次黑便及呕吐。初步判断需进一步检查以明确有无消化道出血及胃部病变。
 # 病史与背景
-- **现病史**：上腹疼痛反复发作4年，每年春季多发，近3个月持续疼痛；疼痛位于心窝处，有烧灼感，进食冷、硬、辛辣食物或工作紧张时诱发，近3个月疼痛可忍受，无夜间痛醒。
-- **黑便史**：近4年出现两次黑便，一次在一年前，一次在三个月前，每次持续约一个月，每日最多两次，大便形状正常，仅颜色改变；两次均住院治疗，住院后两三天大便转黄。
-- **呕吐**：近两个月呕吐数次，吐出黄水样酸味物，为早晨和中午所食食物，晚上腹胀时呕吐后缓解。
-- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，之后体检肝功均正常；无手术史。
-- **过敏史**：小时候因扁桃体发炎在成都市儿童医院就诊，服用磺胺药后左手起红疹，持续半个月，确诊磺胺药过敏。
-- **家族史**：父亲76岁，有低血压；母亲75岁，有冠心病，服药控制良好；有一弟弟，身体健康；有一婶婶患胃癌，但医生解释婶婶无血缘关系，不必担心遗传。
-- **个人史**：出生并长期生活在成都，在成都轻工研究所从事科研工作，工作紧张，经常加班熬夜；吸烟，以前一天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝；喝茶，每天泡两次；26岁结婚，有一小孩，爱人及小孩身体健康。
-- **近期用药**：最初服用“大叔”（可能为“达喜”），效果渐差，从每日两次每次一颗增至每日四五次；后服用奥美拉唑（武汉药厂产）和阿莫西林，以及医务室自配胃炎合剂，效果不佳。
+- **现病史**：上腹疼痛4年，每年春季多发，近3个月反复发作；疼痛位于心窝处，有烧灼感，吃冷、硬、刺激性食物或工作紧张时发作，可忍受，白天为主，夜间无痛醒。
+- **黑便史**：一年前及三个月前各出现一次黑便，持续约一个月，均住院治疗后大便转黄，住院时间约10天及两三天。
+- **呕吐**：最近两个月呕吐数次，吐出黄水样酸味物，晚上腹胀想吐，吐后缓解，无隔夜食物及红色或黑色内容物。
+- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，之后体检肝功均正常；小时候因扁桃体炎在成都市儿童医院就诊。
+- **过敏史**：磺胺药过敏，小时候服用磺胺药后左手起红疹，持续半个月，医生告知不能吃磺胺药。
+- **家族史**：父亲76岁，有低血压（90/60）；母亲75岁，有冠心病，服药控制良好；有一个弟弟，身体健康；一个婶婶患胃癌。
+- **个人史**：吸烟，以前一天一包，现限制在10支以内；偶尔饮酒，平时不喝；每天泡两次茶；工作紧张，经常加班熬夜。
+- **近期用药**：自行服用奥美拉唑（武汉药厂生产）、阿莫西林及所里医务室配制的胃炎合剂，效果逐渐变差，奥美拉唑用量从最初一天两次、每次一颗增至每天四五次。
 # 诊断与检查结果
-医生未给出明确诊断结论，需进一步检查。已安排大便检查以排查出血，并预约后天做胃镜。
+本次就诊未进行相关检查，医生建议留大便检查以明确有无出血，并预约胃镜检查。既往检查结果：16岁患甲肝时在三医院住院，出院时肝功能正常；近期未做过针对腹痛的检查。
 # 治疗方案与医嘱
-- **检查安排**：留大便检查，以排查是否存在消化道出血；胃镜预约在后天进行，因患者爱人可请假陪同。
-- **生活方式**：建议戒烟限酒，因吸烟、饮酒可能加重胃部疾病；注意避免工作紧张、劳累、加班熬夜，因可能诱发或加重病情。
-- **复诊与陪同**：胃镜需有爱人陪同，预约后天；医生将总结病情后向上一级医生张医生汇报，再与患者商量下一步处理意见。
+- **检查安排**：留取大便标本送检，以明确有无消化道出血；预约后天进行胃镜检查，因患者爱人后天可请假陪同。
+- **生活方式**：建议戒烟、少喝酒，因吸烟饮酒可能加重胃部疾病；注意避免工作紧张、劳累和熬夜，这些因素可能诱发或加重病情。
+- **复诊与沟通**：医生将总结病情后向上一级医生张医生汇报，再与患者商量下一步处理意见。
+- **手术问题**：需等检查资料全面后再判断是否需要手术，若药物能控制病情则不需手术。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 大叔（可能为达喜） | 每次一颗 | 每日两次，后增至每日四五次 | 口服 | 效果渐差，需增加剂量 |
-| 奥美拉唑（武汉药厂产） | 未提及 | 未提及 | 口服 | 效果不佳 |
-| 阿莫西林 | 未提及 | 未提及 | 口服 | 效果不佳 |
-| 胃炎合剂（医务室自配） | 未提及 | 未提及 | 口服 | 效果不佳 |
+| 奥美拉唑 | 未提及 | 最初一天两次，每次一颗，现增至每天四五次 | 口服 | 武汉药厂生产，效果逐渐变差 |
+| 阿莫西林 | 未提及 | 未提及 | 口服 | 未提及 |
+| 胃炎合剂 | 未提及 | 未提及 | 口服 | 所里医务室配制 |
 # 复诊与预警信号
-复诊时间：后天做胃镜，具体时间待预约确认。⚠️ 需立即就医的预警症状：原文未提及。</t>
+复诊时间：后天进行胃镜检查，检查后由张医生查房，再与患者商量下一步处理意见。
+⚠️ 预警症状：若再次出现黑便，需立即就医，以明确有无消化道出血。</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>49.3</v>
+        <v>47.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8519/1261</t>
+          <t>8519/1262</t>
         </is>
       </c>
     </row>
@@ -6799,40 +6698,37 @@
       <c r="C18" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行（国开行）与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司（招银租赁）金融借款合同纠纷二审案件，由最高人民法院依法组成合议庭公开开庭审理。庭审围绕三个争议焦点展开辩论：一是国开行对抵押设备是否尽到审查义务、是否构成善意取得，以及融资租赁登记的性质与效力；二是案涉借款的罚息、复利计算方式；三是东源煤电是否应连带给付违约金。合议庭在查明事实、分清是非的基础上提出调解方案，各方当事人均无异议，当庭达成调解协议。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决，向最高人民法院提起上诉。合议庭依法组成并公开开庭审理，围绕动产抵押权与融资租赁所有权冲突、罚息复利计算、违约金三个争议焦点展开法庭调查与辩论。经合议庭评议提出调解方案，各方当事人均无异议，自愿达成调解协议，法院当庭确认并出具调解书。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国开行） | 请求确认对案涉设备享有抵押权，主张利息、罚息、复利计算至2018年6月13日，并主张东源煤电支付违约金。 | 国开行主张其审查义务仅限于抵押人曲靖电力公司，已按人民银行规定查询融资租赁登记系统，未发现登记信息，构成善意取得；利息应自2017年12月21日计算至2018年6月12日，罚息自2018年6月13日起算，复利按合同第六条约定计算；东源煤电未配合办理账户管理及柜台签约手续，构成违约，应支付千分之一违约金。 |
-| 被上诉人（东源电力等） | 请求驳回国开行上诉请求，主张罚息不应计收复利，违约金无合同依据。 | 东源方认为国开行宣布贷款提前到期未给合理期限，不符合合同约定；罚息不应作为复利计算基数，依据人民币利率管理规定第21条及最高人民法院2015年、2016年判例；国开行未举证东源煤电违反柜台协议，且未发出限期纠正通知，不符合合同约定。 |
-| 被上诉人（招银租赁） | 请求确认对涉案六项设备享有所有权，主张国开行不构成善意取得。 | 招银租赁主张其于2012年取得设备所有权，国开行抵押权于2015年设立，时间在后；国开行在抵押时未查询人行征信中心融资租赁登记，不符合2014年93号文要求，不构成善意取得；东源煤电出资系无权处分，工商登记公示的是出资行为而非动产所有权。 |
+| 上诉人（国家开发银行） | 请求改判罚息自2018年6月13日起算，复利按合同约定计算，并主张东源煤电支付违约金。 | 主张已尽审慎义务，构成善意取得；利息计算至2017年12月20日，罚息自2018年6月13日起算，复利自2018年3月21日起算；东源煤电未配合办理账户管理及柜台签约手续，构成违约。 |
 # 举证与法庭调查
 **证据与质证意见**
-- 国开行提交2018年9月对曲靖电力公司的融资租赁查询证书，招银租赁认为不符合2014年93号文要求，国开行在抵押时点未进行相应查询。
-- 国开行提交工商部门出资证明及权属证明，主张已对设备所有权尽到审慎审查义务；招银租赁认为工商登记公示的是出资行为而非动产所有权，东源煤电出资系无权处分。
-- 招银租赁提交回租设备清单（一审证据7页），仅载明设备名称和生产厂家，未提及型号；国开行主张无法据此识别设备唯一性。
-- 招银租赁提交2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行主张该报告已载明设备出资事项。
-- 国开行提交2018年核查表（证据108页），显示曲靖电力公司名下无融资租赁登记；招银租赁认为该核查不符合要求。
+- **东源方提交2015年12月2日邮件**：主张已告知国开行设备融资租赁情况，国开行应尽注意义务。国开行质证称邮件正文及附表均未提及融资租赁，且抵押设备为通用设备，无法唯一识别。
+- **国开行提交2018年9月查询证书**：主张已查询融资租赁登记系统。招银租赁质证称该查询不符合201493号文规定，且查询时点晚于抵押登记时点。
+- **招银租赁提交回租设备清单**：主张设备已登记。国开行质证称清单仅载明设备名称和生产厂家，未载明型号，无法确认同一设备。
+- **国开行提交工商出资证明及权属证明**：主张已尽审慎义务。招银租赁质证称工商登记公示的是出资行为而非动产所有权。
 **法官询问要点**
 - 合议庭询问各方对中国人民银行征信中心融资租赁登记性质及法律后果的理解。
-- 询问国开行贷款前审查是否有内部规定要求查询融资租赁登记，未查到结果时是否保留筛查记录。
-- 询问招银租赁在融资租赁登记系统中是否登记设备唯一标识码，该标识码是否为必填项。
-- 询问国开行和招银租赁关于查询通知规定的性质及违反后果。
+- 询问国开行贷款前审查是否内部规定必须查询融资租赁登记系统，未查到结果是否需保留单据。
+- 询问融资租赁登记系统中设备唯一标识码是否必填项。
+- 询问查询通知规定违反后是否导致最高人民法院相关司法解释的适用。
 - 询问各方对因不同登记机构产生登记瑕疵的看法及建议。
 **双方辩论的争议焦点**
-- 国开行是否尽到审查义务、是否构成善意取得：国开行主张审查义务仅限于抵押人曲靖电力公司，已按人民银行规定查询系统，未发现登记信息；招银租赁认为国开行未在抵押时查询，不构成善意。
-- 融资租赁登记的性质与效力：国开行认为是行业强制性规范，招银租赁及东源方认为是行业指导性规范，不产生物权效力。
-- 设备唯一标识码与查询方式：招银租赁称暗设五套设备无唯一识别码，未登记；国开行称查询曲靖电力公司无融资租赁登记，但未保留查询记录。
+- **争议焦点一：动产抵押权与融资租赁所有权冲突**。国开行主张已尽审慎义务，构成善意取得；招银租赁认为国开行未在抵押时查询融资租赁登记，不构成善意；东源方主张邮件已告知。
+- **争议焦点二：罚息、复利计算**。国开行主张罚息自2018年6月13日起算，复利按合同约定计算；东源方认为罚息不应作为复利基数，且贷款提前到期应给合理期限。
+- **争议焦点三：违约金**。国开行主张按合同第24条第三项支付千分之一违约金；东源方认为国开行未举证违约且未发出限期纠正通知。
 # 庭审结果
-本案争议焦点为：一是国开行对抵押设备是否尽到审查义务、是否构成善意取得，以及融资租赁登记的性质与效力；二是案涉借款的罚息、复利计算方式；三是东源煤电是否应连带给付违约金。合议庭休庭评议后宣读调解方案，各方均无异议并签字确认。调解方案主要内容包括：确认国开行对东源公司债权扣除破产清偿本金外，利息、罚息、复利合计6474.4513万元；确认招银租赁对涉案六项设备享有所有权，对应债权1377.4137万元；确认国开行对93项设备有抵押权；招银租赁和国开行对案涉全部发电设备整体盘活处置，变现价格及实现费用双方各担50%；变现款不足清偿时按破产重整计划预留方案实现；若司法变现不能，双方权益实现后均放弃对案涉设备权益，由东源曲靖电力自主生产经营。一审判决第二项、第四项无争议，按判项内容在调解书中确认；诉讼费按规定确定。合议庭指出，动产抵押权与融资租赁物所有权冲突是司法实践中的普遍性难题，根本原因在于国家尚未建立统一的动产登记制度，现有融资租赁登记系统和动产抵押登记系统缺乏有效衔接，将向有关部门提出司法建议。</t>
+本案争议焦点为：一、动产抵押权与融资租赁所有权冲突；二、罚息、复利计算；三、违约金。经合议庭评议，提出调解方案，各方当事人均无异议，自愿达成调解协议。调解方案主要内容：确定国开行对东源公司债权扣除破产清偿本金外，利息、罚息、复利共计6474.4513万元；确定招银租赁对涉案六项设备享有所有权，对应债权数额1377.4137万元；确定国开行对93项设备有抵押权，招银租赁对六项设备有所有权；双方对案涉全部发电设备整体盘活处置，变现价格及费用各担50%；若司法变现不能，双方均放弃对案涉设备权益，由东源曲靖电力自主生产经营。各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认。一审诉讼费按一审判决执行，二审诉讼费由本院依法确定。各方之间就本案涉及问题不再存在任何争议。</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>64.59999999999999</v>
+        <v>167.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30731/2113</t>
+          <t>30731/1523</t>
         </is>
       </c>
     </row>
@@ -6939,44 +6835,38 @@
       <c r="C19" t="inlineStr">
         <is>
           <t># 候选人概况与面试岗位
-本次面试为公务员结构化面试，共20分钟，考生需回答4个问题，考察综合分析、组织协调、应急处理和公共服务能力。面试由考官主持，计时员计时，考生逐题作答，全程无补充。
-第一题以绳子对骏马、风筝、陀螺的启示为引，考生从自我反省、单位风气、权利责任、工作动力四方面阐述公务员工作启示，引用曾子“吾日三省吾身”，提出单位应形成紧张、活泼、团结、有趣的风气，并强调权利与责任需平衡。第二题为AI企业调研任务，考生提出前期准备、制定方案、实施调研三步走，调研涵盖市场状况、服务需求、管理措施三方面，具体方式包括企业对接、调查问卷、座谈会，并提及人才引进、政策倾斜、用地审批等需求。第三题模拟答复记者关于排水管道反复堵塞的投诉，考生解释管道为上世纪90年代修建、老城区改造难度大、夏季用水高峰问题集中，承认工作失职，承诺立即联系维修师傅现场维修，并已向上级汇报，计划通过城市综合保障工程改善硬件。第四题针对城市改造工程扰民矛盾，考生区分主要矛盾（时间需求不满足）与次要矛盾（噪音、出行、舆论），提出督促施工方加快进度、防噪墙、洒水降尘、替代道路、交通广播推荐路线、鼓励公交出行、增加公交班次、公告公开透明沟通等措施。
+本次面试为公务员结构化面试，时长20分钟，共4题，由计时员计时、考官提问、考生逐题作答。面试围绕绳子哲理对公务员工作的启示、AI企业调研任务、处理记者投诉、雨污分流工程社会矛盾四个议题展开，旨在考察考生的综合分析、组织协调、应急处理和公共服务能力。考生在四题中均能结合具体情境展开论述，逻辑清晰，措施具体，展现了较强的综合分析、组织协调与应急处理能力。面试过程中，计时员在第四题作答期间提醒剩余3分钟，考生未作补充，面试按时结束。
 # 面试问答纪要
 ## 第一题（综合分析能力）
-- **题目**：以绳子对骏马、风筝、陀螺的启示，谈对做好公务员工作的启示。
-- **作答要点**：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；引用曾子“吾日三省吾身”强调自我反省；提出单位应形成紧张、活泼、团结、有趣的风气，同事间比能力和效率而非票子、车子、房子；治国理政中权利是“风”、责任是“绳子”，需建立权利清单、责任清单；公职人员工作需“连轴转”，靠责任感和成就感支撑，如撰写长材料时加班加点、斟词酌句。
+- **题目**：骏马、风筝、陀螺与绳子的关系蕴含丰富人生哲理，谈谈对做好公务员工作的启示。
+- **作答要点**：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；引用曾子“吾日三省吾身”强调自我反省；单位应形成紧张、活泼、团结、有趣的风气，同事间比能力效率而非票子车子房子；治国理政中权力与责任是风筝的绳，需建立权力清单、责任清单；陀螺的“连轴转”体现公职人员的责任感和成就感，撰写材料加班加点、斟词酌句是常事。
 ## 第二题（组织协调能力）
-- **题目**：作为市政府办公室工作人员小王，负责调研本市AI相关企业发展状况和服务需求，为出台扶持政策提供依据。
-- **作答要点**：前期准备包括利用业余时间补课充实AI知识、学习兄弟城市调研经验、查阅国务院及省厅关于人工智能发展的指导意见；制定工作方案，分客观（企业发展现状）和主观（政府服务需求）两方面；调研分三部分：市场状况、服务需求、管理措施；具体方式包括与企业对接阅读发展报告、制定调查问卷请专家学者修改、召开人工智能企业座谈会；服务需求涉及人才引进、政策倾斜、用地审批、人才长效培养机制；管理措施关注AI发展中的问题，如共享充电宝信任危机，需及时纠偏。
+- **题目**：作为市政府办公室工作人员小王，负责调研本市AI企业发展状况和服务需求，为出台扶持政策提供依据，如何完成？
+- **作答要点**：前期准备包括学习兄弟城市调研经验、查阅国务院及省厅关于人工智能的指导意见、利用课余时间补课充实知识储备；制定包含客观（企业发展现状）和主观（政府服务需求）两方面的工作方案，呈报领导审阅后实施；具体措施包括阅读企业报告、制定调查问卷并请专家修改、召开人工智能企业座谈会、问卷调查管理措施；提到AI发展可能带来问题，如共享充电宝的信任危机，需及时纠偏。
 ## 第三题（应急处理能力）
-- **题目**：作为市级服务标兵小王，现场模拟答复记者关于居民投诉排水管道反复堵塞的问题。
-- **作答要点**：解释管道为上世纪90年代修建，老城区改造难度大，夏季用水高峰问题集中；承认工作失职，请求媒体给予改进机会；已联系维修师傅，准备赶到现场维修；已向上级汇报，计划通过城市综合保障工程完善硬件；希望媒体向公众解释政府难处和管道真正存在的问题。
+- **题目**：记者投诉管道疏通后再次堵塞，质疑标兵名不副实，现场模拟答复。
+- **作答要点**：解释管道为上世纪90年代修建，老城区改造难度大，夏天用水高峰导致问题集中出现；承诺立即联系维修师傅赶赴现场维修；已将硬件问题汇报上级部门，计划通过城市综合保障工程改善基础设施；承认工作失职，请求媒体给予改进机会，并希望媒体向公众解释政府难处和管道问题。
 ## 第四题（公共服务能力）
-- **题目**：从公共服务角度谈谈处理道路改造和雨污分流工程引发社会矛盾的思路。
-- **作答要点**：区分主要矛盾（时间上需求不满足）和次要矛盾（噪音、出行、舆论）；督促施工方加快进度，保证质量；采取防噪墙、洒水降尘减少噪音和灰尘；建议使用替代道路、交通广播推荐路线、鼓励公交出行、增加公交班次和频率；以公告形式在网络上公开透明沟通，获得市民理解和支持。
+- **题目**：道路改造和雨污分流工程带来噪音、灰尘、交通拥堵等问题，居民不满，从公共服务角度谈处理社会矛盾的思路。
+- **作答要点**：分析主要矛盾是时间上的需求不满足，次要矛盾是噪音、出行、舆论问题；措施包括督促施工方加快进度、加防噪墙、洒水降尘、建议便道、通过交通广播推荐路线、引导公交出行、增加公交班次；计划以公告形式在网络上公开透明发布信息，获得市民理解和支持。
 # 能力评估
 | 评估维度 | 推荐评级 | 评估依据（具体事例） |
 | --- | --- | --- |
-| 专业/技术能力 | 良 | 第一题能结合绳子对骏马、风筝、陀螺的启示，从自我反省、单位风气、权利责任、工作动力等多角度阐述公务员工作启示，引用曾子“吾日三省吾身”；第二题调研任务中提出学习兄弟城市经验、查阅国务院及省厅文件，体现政策理解能力。 |
-| 项目经验 | 中 | 第二题调研任务中提出企业对接、调查问卷、座谈会等方式，但未提及具体项目经历或数据；第三题模拟处理排水管道投诉，体现一定实务经验，但细节较笼统。 |
-| 沟通协作 | 良 | 第三题现场模拟答复记者，能解释管道问题原因、承认失职、承诺维修，并希望媒体解释政府难处；第四题提出通过公告公开透明沟通，体现与公众沟通意识。 |
-| 岗位匹配度 | 良 | 四题均围绕公务员工作场景，考生能结合自身角色（如片区负责人、市政府办公室工作人员）作答，体现岗位认知；但部分措施偏理想化，如“城市综合保障工程”未说明具体实施路径。 |
-| 问题解决能力 | 良 | 第三题针对管道反复堵塞，提出立即维修、向上级汇报、争取长期改善；第四题针对扰民矛盾，提出加快进度、防噪降尘、替代道路、公交出行等措施，但部分措施缺乏量化指标。 |
-| 思维逻辑性 | 良 | 第一题从绳子对骏马、风筝、陀螺的启示分层展开；第二题调研任务分前期准备、制定方案、实施调研三步；第四题区分主要矛盾和次要矛盾，逻辑清晰。 |
-| 应变能力 | 良 | 第三题面对记者质疑，能冷静解释原因、承认失职、提出补救措施；第四题面对居民不满，能区分矛盾并逐一提出对策，但未涉及突发情况应对。 |
-| 语言表达 | 中 | 答题流畅但口语化较重，如“连轴转”多次出现，部分表述重复；第三题模拟对话中“咱们”等口语词较多，正式场合表达需更精炼。 |
+| 项目经验 | 良 | 第二题中提出调研的具体步骤，包括阅读企业报告、制定调查问卷、召开座谈会等，体现对调研流程的熟悉；第三题中能解释管道为上世纪90年代修建、老城区改造难度大，体现对基层工作的了解。 |
+| 沟通协作 | 良 | 第三题中现场模拟答复记者，能解释管道问题、承诺立即维修、请求媒体给予改进机会，体现一定的沟通能力；第四题中提出通过公告形式在网络上公开透明发布信息，体现与公众沟通的意识。 |
+| 问题解决能力 | 良 | 第四题中针对雨污分流工程矛盾，提出督促施工方加快进度、加防噪墙、洒水降尘、建议便道、交通广播推荐路线、引导公交出行、增加公交班次等多项具体措施，体现较强的问题解决能力。 |
 # 综合素质
-- **突出亮点**：综合分析能力较强，第一题能从绳子对骏马、风筝、陀螺的启示引申出自我反省、单位风气、权利责任、工作动力等多维度思考，并引用曾子名言；组织协调思路清晰，第二题调研任务分前期准备、制定方案、实施调研三步，涵盖市场、服务、管理三方面；应急处理有担当，第三题承认工作失职并承诺立即维修，同时向上级汇报争取长期改善。
-- **潜在风险点**：部分表述口语化且重复，如“连轴转”多次出现；第二题调研措施偏笼统，如“调查问卷”未说明具体发放范围和样本量；第四题对舆论引导的论述较简略，仅提及公告形式，未涉及具体舆情应对策略。
-- **推进建议**：若进入下一轮，建议考生加强答题的条理性，减少口头禅和重复；调研类题目可补充具体数据或案例支撑；应急处理类题目可增加与媒体、居民的互动细节，体现更全面的沟通技巧。</t>
+- **突出亮点**：考生在四题中均能结合具体情境展开论述，如第一题引用曾子名言、第二题提出具体调研步骤、第三题现场模拟答复记者、第四题提出多项具体措施，逻辑清晰，措施具体。
+- **潜在风险点**：考生在第二题中自述对人工智能存在知识盲区，需利用课余时间补课；第三题中承认工作失职，请求媒体给予改进机会，可能暴露应急处理中的不足。
+- **推进建议**：建议考生在后续工作中加强专业知识学习，提升对高新技术产业的理解；在应急处理中更注重事前预防和事后跟进，减少类似投诉事件的发生。</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>58.7</v>
+        <v>53.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5808/2598</t>
+          <t>5808/1738</t>
         </is>
       </c>
     </row>
@@ -7045,65 +6935,67 @@
       <c r="C20" t="inlineStr">
         <is>
           <t># 参观概况
-本次参观为故宫博物院游览，讲解围绕午门、太和殿、乾清宫等主要景点展开，核心主题为故宫历史建筑与游览攻略。讲解从午门开始，沿中轴线依次介绍太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、延禧宫、御花园至神武门，全程覆盖前朝与后宫区域。讲解内容涵盖各建筑的历史功能、建筑特色、相关典故及游览注意事项，并标注了七处免费盖章点与三条推荐游览路线。
+本次参观为故宫博物院游览攻略讲解，由导游（发言人1）以视频形式系统介绍故宫主要景点、历史典故、免费盖章点及游览路线。讲解覆盖午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、翊坤宫、永寿宫、太极殿、慈宁宫、寿康宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、珍妃井、东筒子夹道、延禧宫、景仁宫、御花园、神武门等约27处景点，全程约12分钟，以中轴线为主干、穿插东西两侧支线，形成完整游览动线。
+讲解核心围绕建筑规制与历史功能展开，如午门“明三暗五”门洞规制、太和殿盛大典礼功能、保和殿殿试考场沿革等，并穿插皇帝立储、慈禧居住等历史典故。导游同时汇总**七个免费盖章点**（合计22枚免费印章）、**三条游览路线**（分别约2小时、半天、全天）及紫禁城100购买与盖章规则，供游客按时间与体力自行选择。
 # 核心看点与讲解
-- **午门**：讲解“明三暗五”结构，三个门洞进门后变五个；中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，两侧门走皇亲国戚和文武百官。明朝皇帝在此杖打犯错大臣，清朝皇帝在此颁发次年历书（颁朔之礼）。
-- **太和门广场**：有五座金水桥，皇帝走中间，黄金国器走挨着中间两座，文武百官走最边上。太和门为明朝御门听政（上朝）之处，门口铜狮子是故宫六对铜狮中最大的一对，脚踩寰宇象征权力，建议单独拍照而非站在其下合影。
-- **太和殿**：即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封，文武百官在太和殿广场高呼“吾皇万岁万岁万万岁”，站位遵循“文东武西”原则。西边红衣阁为皇帝银库，东边体仁阁为缎库。
+- **午门**：排队检票处，明朝皇帝在此杖打犯错大臣，清朝皇帝在此颁发次年历书（颁朔之礼）。门洞呈“明三暗五”规制——正面看三个门洞，进门后变五个；中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，两侧门洞走皇亲国戚和文武百官。
+- **太和门广场**：眼前有五座金水桥，皇帝走中间桥，黄金国器走挨着中间的两座桥，文武百官走最边上。太和门是明朝皇帝御门听政（上朝）的地方，门口铜狮子为故宫六对铜狮中最大的一对，脚踩寰宇象征权力，建议单独拍照即可，不宜站在其下合影。
+- **太和殿**：即金銮殿，但并非上朝场所，而是举行盛大典礼之地，如皇帝登基、皇后册封，文武百官在太和殿广场朝拜。百官站位遵循“文东武西”——文官站东边，武官站西边；西边红衣阁是皇帝银库，东边体仁阁是缎库。
 - **中和殿**：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再前往太和殿。
-- **保和殿**：自乾隆五十四年起为殿试考场；东北角汉字馆有4枚免费印章，可购买《紫禁城100》现场盖章，每家店印章不同，购买后不能去其他店铺盖章，汉字馆印章数量最多，可邮寄到家或自行携带。
-- **乾清门**：过此门即后宫（皇帝与妃嫔生活区域），皇帝在此上早朝；东边九卿直房为等级高的大臣等待召见处，西边为军机处。门口铜狮耳朵耷拉、眉毛遮眼，警示后宫之人“不该看的别看，不该听的别听”。
-- **乾清宫**：皇帝寝宫，内有27张龙床，据说是为防止刺客找到皇帝位置；牌匾“正大光明”后藏立储诏书，皇帝写两份诏书，驾崩后对比验证是否被动过手脚。门口有铜鹤、铜龟及紫禁城最小宫殿“社稷江山金殿”，提醒皇帝将江山社稷放在第一位。
-- **交泰殿**：存放25块传国玉玺。
-- **坤宁宫**：皇后居所，明朝所有皇后均住于此；东北角文创店有5枚免费印章。
-- **储秀宫**：慈禧住了20多年的地方，现为慈禧五十大寿时期原状陈列，因其子在此出生而受喜爱；旁边文创店有3枚免费印章。
-- **翊坤宫、永寿宫、太极殿**：永寿宫西边为东西六宫中唯一被称为“殿”的太极殿。
-- **慈宁宫、寿康宫**：慈宁宫为康熙给奶奶孝庄皇太后修建的养老院，寿康宫为甄嬛居住地。
-- **冰窖书吧**：有3枚免费印章，印章造型有批折子的感觉，可购买冰溪图。
-- **断虹桥**：网红打卡地，石狮子形态各异，最有名的为“武当狮”。
+- **保和殿**：自乾隆五十四年起为科举考试殿试考场。东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》并现场盖章；故宫多处可购此书，但每家店印章不同，从汉字馆购买后不能去其他店铺盖章，汉字馆印章数量据称最多，盖完可邮寄到家或自行带走。
+- **乾清门**：过此门即后宫（皇帝与妃嫔生活区域）。东边九卿直房是等级高的大臣等待皇帝召见之处，西边为军机处。门口铜狮耳朵耷拉、眉毛遮眼，意在警示后宫之人“不该看的别看，不该听的别听”。
+- **乾清宫**：皇帝平时睡觉之处，内有27张龙床，据说是为防止刺客找到皇帝位置。牌匾“正大光明”后藏皇帝立储秘密——皇帝写两份立储诏书，一份藏于牌匾后，驾崩后两份对比，名字不一致即说明诏书被动过手脚。门口有铜鹤铜龟及紫禁城最小宫殿“社稷江山金殿”，提醒皇帝将江山社稷、百姓民生放在首位。
+- **交泰殿**：内放25块传国玉玺。
+- **坤宁宫**：住皇后的宫殿，明朝所有皇后都住于此。东北角文创店有5枚免费印章。
+- **储秀宫**：慈禧住了20多年的地方，现为慈禧五十大寿时期原状陈列，慈禧喜欢此处因其子在此出生。旁边文创店有3枚免费印章。
+- **翊坤宫、永寿宫、太极殿**：翊坤宫和永寿宫为东西六宫建筑，永寿宫西边是东西六宫中唯一被称为“殿”的太极殿。
+- **慈宁宫、寿康宫**：慈宁宫是康熙为奶奶孝庄皇太后修建的养老院，旁边寿康宫为甄嬛（《甄嬛传》人物）居住地。
+- **冰窖书吧**：有3枚免费印章，印章造型好，盖章时有批折子的感觉。
+- **断虹桥**：网红打卡地，桥上石狮子形态各异，最有名的是“捂裆狮”。
 - **武英殿**：后改为陶瓷馆，目前关闭状态，只能在门口观看。
-- **文华殿**：与武英殿对应“文东武西”，参观时未开放，据说有展览。
-- **箭亭**：清朝皇帝及子孙练习骑马射箭之处，旁边商店可购买文创雪糕。
-- **钟表馆**：展示古代钟表造型。
-- **珍宝馆（宁寿全宫）**：门口为我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据说是烧制琉璃砖瓦弄坏后工匠用木头刷白漆以假乱真。珍宝馆并非单独展厅，院子周围屋子均为展区；此处为乾隆给自己修建的养老院，退休后未放权仍照常上朝办公。皇极殿1:1复刻乾清宫，宁寿宫对标坤宁宫，乐寿堂为故宫唯一能进去参观的皇家寝室，有二龙仙楼设计；珍妃井为当年慈禧将珍妃丢入之处，现井口石非珍妃进入的入口。出口商店有3枚免费印章。
-- **东筒子夹道**：拍照出片的长夹道。
-- **延禧宫、景仁宫**：延禧宫为网红打卡地，景仁宫为甄嬛被封熹妃时所住，珍妃也曾居住。
-- **御花园**：钦安殿供奉真武大帝，紫禁城靠山景山从天上酷似闭目盘坐人像，有人说该造型即真武大帝。
-- **神武门**：故宫北门，出门左手边有两个盖章点——角楼咖啡2枚免费印章、故宫文创2枚免费印章。
+- **文华殿**：与武英殿对应“文东武西”，导游去时未开，据说现有一个展览。
+- **箭亭**：清朝皇帝及子孙练习骑马射箭之处，旁边商店可买文创雪糕。
+- **钟表馆**：展示古代钟表造型，令人开眼界。
+- **珍宝馆**：强烈建议参观，实为宁寿全宫，是乾隆给自己修建的养老院，乾隆退休后未放权仍照常上朝。馆前有我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头——据传当年烧制琉璃砖瓦时弄坏一块，工匠为保命用木头刷白漆以假乱真。馆内并非单独展厅，院子周围屋子都值得参观，凤冠展品游客极多。皇极殿据称1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后为乐寿堂——故宫内唯一能进去参观的皇家寝室，有二龙戏珠设计，让人联想到恭王府和珅卧室。
+- **珍妃井**：慈禧当年把珍妃丢进去之处，现井口石非珍妃进入的原口。
+- **东筒子夹道**：长长的夹道，拍照非常出片。
+- **延禧宫、景仁宫**：延禧宫为网红打卡地，景仁宫是甄嬛被封熹妃时所住，珍妃也住过。
+- **御花园**：内有钦安殿，供奉真武大帝；紫禁城靠山景山从天上看酷似闭目盘坐人像，有人说该造型就是真武大帝。
+- **神武门**：故宫北门，游览终点。出门左手边有两个盖章点——角楼咖啡（2枚免费印章）和故宫文创（2枚免费印章）。
 # 互动与体验
-- **盖章互动**：讲解中标注了七处免费盖章点，包括保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫旁文创店3枚、冰窖书吧3枚、珍宝馆出口商店3枚、神武门外角楼咖啡2枚及故宫文创2枚免费印章。
-  - **汉字馆**：可购买《紫禁城100》并现场盖章，工作人员现场操作，印章数量为各店最多；购买后不能去其他店铺盖章，需有所取舍。
-  - **冰窖书吧**：印章造型独特，盖章时有“批折子”的感觉；讲解者在此购买了冰溪图。
-- **文创雪糕**：箭亭旁商店可购买文创雪糕，讲解者以提问方式引导观众猜测雪糕造型人物，并邀请在评论区分享。
-- **拍照打卡**：太和门铜狮子造型威武，讲解者建议单独拍张照即可，不建议站在狮子底下合影；东筒子夹道拍照非常出片，是很多游客喜欢来的打卡地。
-- **个人感受**：钟表馆展品造型令人“开了眼”；珍宝馆内宝贝惊艳，但游客太多，尤其是看凤冠的区域“没点技术还真挤不进去”；珍宝馆是故宫唯一能进去参观皇家寝室（乐寿堂）的地方。
+- **盖章互动**：导游全程标注了**七个免费盖章点**，并提示喜欢盖章的游客可截图保存位置。各点印章数量分别为：保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫边文创店3枚、冰窖书吧3枚、珍宝馆出口右手边商店3枚、神武门出门左手边角楼咖啡2枚、神武门出门左手边故宫文创2枚。
+  - **汉字馆盖章**：位于保和殿东北角，有4枚免费印章，可购买《紫禁城100》由工作人员现场盖章。导游评价“这感觉真是盖了帽了”，并调侃“怪不得乾隆那么喜欢盖章”。
+  - **购买限制**：故宫内多处可购买《紫禁城100》，但每家店印章不同，从汉字馆购买后不能去其他店铺盖章，导游提醒“注定得有所取舍”，并称汉字馆印章数量最多。
+  - **冰窖书吧盖章**：位于慈宁宫、寿康宫南侧，有3枚免费印章。导游称印章造型好，盖章时有“批折子的感觉”，并在此购买了冰溪图。
+  - **珍宝馆出口商店盖章**：从珍宝馆出口出来后右手边往里走有商店，有3枚免费印章，导游提醒别漏掉。
+- **文创雪糕体验**：箭亭旁商店可购买文创雪糕，导游以提问方式互动：“有谁知道他是谁吗？欢迎在评论区分享一波。”
+- **拍照打卡点**：导游多次提示适合拍照的位置，包括太和门铜狮子（建议单独拍张照即可，不宜站在其下方合影）、东筒子夹道（“拍照非常出片”，受小姐姐们喜爱）、断虹桥（可寻找形态各异的石狮子中著名的“武当狮”）。
+- **珍宝馆参观体验**：导游强烈建议参观珍宝馆，称“每一样都能让您忍不住说出平时常用的感叹词”，但提醒游客众多，尤其是看凤冠的“没点技术还真挤不进去”。
+- **乐寿堂体验**：位于珍宝馆区域内，是故宫里**唯一能进去参观的皇家寝室**，可见二层仙楼设计，导游提示可联想到恭王府和珅的卧室。
+- **个人游览数据**：导游按第一条路线走完全程，一天走了**3万步**，并提醒游客游览过程中“别忘了适当休息和补充水分”。
 # 收获与建议
-- **择时与排队**：建议早起排队，一进门就沿中轴线往里冲，可错开大批旅游团人群；等大部队到达时，已能在人少时逛完最重要的几个景点。讲解者实测进门一小时后游客明显增多。
-- **路线选择**：提供三条游览路线，按时间与体力自行选择。
-  - **全天路线**：走完视频内所有景点，适合打算在故宫待上一整天的游客，全程约3万步。
-  - **半天路线**：沿中轴线至坤宁宫后，参观景仁宫、延禧宫、钟表馆、珍宝馆，再至御花园，从神武门出，约半天时间。
-  - **省力路线**：沿中轴线至坤宁宫后去储秀宫，再至御花园，从神武门出，约2小时，适合时间有限、不想走太多路的游客。
-- **盖章点汇总**：讲解共标注**7处**免费盖章位置，各点印章数量与特色不同。
-  - **保和殿东北角汉字馆**：4枚免费印章，可购买《紫禁城100》现场盖章，据称印章数量最多。
-  - **坤宁宫东北角文创店**：5枚免费印章。
-  - **储秀宫旁文创店**：3枚免费印章。
-  - **冰窖书吧**：3枚免费印章，盖章时有批折子的感觉。
-  - **珍宝馆出口商店**：3枚免费印章。
-  - **神武门外角楼咖啡**：2枚免费印章。
-  - **神武门外故宫文创店**：2枚免费印章。
-- **盖章注意事项**：故宫内不止一处可购买《紫禁城100》，但每家店印章不同，购买后不能去其他店铺盖章，需提前做好取舍。
-- **饮食与休息提醒**：全天路线一天走3万步，游览过程中需适当休息和补充水分。
-- **拍照建议**：太和门门口铜狮子造型威武，但站在其底下时爪子正好盖在头顶，建议单独给狮子拍照即可，不必合影。
-- **珍宝馆参观提示**：珍宝馆并非单独展厅，院子周围各屋均需入内参观；游客较多，尤其看凤冠处拥挤，需有耐心挤进去。
-- **其他提示**：陶瓷馆（武英殿）目前关闭，只能在门口看看；文华殿讲解者到访时未开放，据称现有一个展览可关注。</t>
+- **择时与排队**：建议早来排队，一进门就沿中轴线往里冲，可错开大批旅游团人群；导游本人一天走了3万步，游览中需注意适当休息和补充水分。
+- **路线选择**：共三条路线可选——第一条走完视频内所有景点，适合打算在故宫待一整天的游客；第二条沿中轴线看坤宁宫后去景仁宫、延禧宫，再逛钟表馆和珍宝馆，出御花园从神武门出，约半天时间；第三条沿中轴线看坤宁宫后去储秀宫，出御花园从神武门出，约2小时，最省力。
+- **盖章点汇总**：共七个免费盖章位置——保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫边文创店3枚、冰窖书吧3枚、珍宝馆出口右手边商店3枚、神武门出门左手边角楼咖啡2枚、神武门出门左手边故宫文创2枚。
+- **紫禁城100购买提示**：故宫里不止一处可购买紫禁城100，每家店印章不同；从汉字馆购买后不能去其他店铺盖章，需有所取舍；汉字馆印章数量据说是最多的，盖完可选择邮寄到家或自行携带。
+- **拍照建议**：太和门门口铜狮子是故宫六对铜狮中最大的一对，但建议单独给狮子拍照即可，不要站在狮子底下合影，因大爪子正好盖在头顶上。
+- **珍宝馆参观提示**：珍宝馆并非单独展厅，院子周围屋子都值得进去看；游客非常多，尤其是看凤冠的区域，需有技术才能挤进去。
+- **陶瓷馆状态**：武英殿已改为陶瓷馆，但目前处于关闭状态，只能在门口看看。
+- **文华殿展览**：导游去时文华殿未开放，据说现在有一个展览，感兴趣可前往观看。
+- **文创雪糕**：箭亭旁边商店可购买文创雪糕，导游未指明雪糕造型对应人物，欢迎在评论区分享。
+- **断虹桥打卡**：断虹桥是网红打卡地，桥上石狮子形态各异，最有名的是武当狮，可自行寻找位置。
+- **东筒子夹道**：从珍宝馆出口出来后的长夹道，拍照非常出片，是很多游客喜欢来的地方。
+- **延禧宫与景仁宫**：延禧宫为网红打卡地，景仁宫是当年甄嬛被封为熹妃时居住的地方，珍妃也住过。
+- **寿康宫打卡**：寿康宫是甄嬛居住的地方，喜欢看《甄嬛传》的游客可到此打卡。
+- **珍妃井说明**：珍妃井上现放的叫井口石，珍妃并非从那个小眼进去的。</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>47</v>
+        <v>57.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4497/2974</t>
+          <t>4497/3773</t>
         </is>
       </c>
     </row>
@@ -7248,56 +7140,60 @@
       <c r="C21" t="inlineStr">
         <is>
           <t># 访谈概况
-本次访谈以留守老人养老问题为核心议题，由主持人实地走访农村与城市两地，访问村政府干部、民政局工作人员、社区社工及多位留守老人本人，旨在了解农村与城市留守老人的生活现状、养老政策落地情况、社工服务困境，并收集各方对改善养老问题的建议。访谈整体反馈基调偏于沉重与务实：农村老人普遍面临子女外出务工导致的独居、经济困难、就医不便与精神孤独，城市社区虽已建立志愿者帮扶与养老服务中心，但社工行业面临工资低、专业欠缺、项目资金不稳定等现实困境。据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住；农村60岁以上老人约73万，占当地人口17.8%，五保户分散供养每月生活费475元，农村老人每月养老金118元。
+本次访谈由主持人（发言人1）以实地走访形式展开，围绕农村与城市留守老人养老问题，先后访问了农村留守老人、村政府与民政局干部（发言人2、发言人4）以及城市社区养老社工（发言人8），旨在呈现留守老人独居现状、了解现行养老政策与实践并寻求解决思路。访谈覆盖三大板块：留守老人生活困境（含独居、就医、经济困难及意外风险）、农村养老政策落实（五保户供养、最低生活保障、党员志愿活动）与城市社区养老实践（志愿者制度、养老服务中心、社工服务）。整体反馈基调为：问题严峻但各方已在探索应对——农村方面政策覆盖基本到位但运营经费难以为继，城市方面社区志愿活动活跃但专业社工供给不足、流失率高。关键数据包括：**65.5%** 的老人子女长期不在身边而独居，仅 **26.8%** 与子女同住；当地老年人口占比 **17.8%** 且预计继续上升；分散供养五保户月生活费 **475元**，农村老年人月养老金 **118元**。
 # 核心反馈
-## 村政府干部（发言人2）
-- **独居规模**：据公安数据，2021年农村60岁以上老人约73万，占17.8%，且因1962–1965年职工档案出生人口多、去年开始退休，预计老龄化程度会越来越严重。
-- **经济困难**：本地经济不发达，老人生病、锻炼等面临经济困难，是留守老人三大问题之一。
-- **子女缺位**：子女不在身边，老人一旦生病住院就比较麻烦，缺乏亲人陪伴。
-- **娱乐匮乏**：老人娱乐方式少，只能坐在一起聊天、打牌。
-- **设施运营断档**：曾探索在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续没有支持，非一次性投入可解决。
-- **五保户供养**：集中供养的五保户将生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养五保户每月发475元生活费，另有护理补贴。
-- **改善建议**：一是请专业施工人进行陪伴；二是倡导在外务工子女多与老人联系；三是丰富老人文化生活、增加娱乐方式；四是希望老年协会专项执行、专门建养老设施，有固定场地，定期开展板报宣传或健康知识讲座，并保障持续运营经费。
-## 民政局干部（发言人4）
-- **五保户待遇**：五保户每月生活费加食补电补共600来块钱，农村生活艰苦，五六百元基本能满足，但大吃大喝不行。
-- **医疗保障**：五保户有病可到卫生院，吃的住的都包。
-- **残疾人保障**：一级二级残疾人按国家政策纳入最低生活保障，分160、270、380元三个标准，视家庭状况制定，最起码保证最低生活保障。
-- **养老金不公**：农村60岁以上老人每月养老金118元，还要提高一点；农村老人与工人养老金待遇完全不一样，但现在的老年人不公平——60年代的人结婚砍树要交砍伐金、杀猪要交屠宰税。
-- **基层探访**：靠村支两委、志愿者上门串门宣传政策、搞卫生，每月开党员组织会，下午到孤寡老人、留守老人家里走一圈。
-## 社区社工（发言人8）
-- **志愿者帮扶**：社区志愿者制度做得较好，前几年划分一对一帮扶，志愿者发现老人住自家楼下就天天去看，老人身体不好时天天送菜。
-- **激励留存**：定期表彰、志愿者积分兑换，年底可到雷锋超市兑换礼品，让志愿者长期坚持；同时发掘偏中年志愿者，今年做“小手拉大手”从儿童青少年入手拉动家长加入。
-- **社区活动**：这周四准备开展送春联活动，邀请书法老师写对联、孩子上门送；去年中秋做月饼，还做过百家宴，让老人感觉社区是大家庭。
-- **自治目标**：之前每次活动由社区策划开展，2023年目标是家长自己组织、社区作为协助者。
-- **心理个案**：曾帮助一位心理问题老人，他与邻里关系不和谐、半夜摔门，志愿者上门但老人抗拒，觉得周围人陌生、没有关心他的人，内心有仇恨式情绪；经长期照料后与邻里关系好转、能接受建议，但今天还打电话说寂寞空虚、得不到关注。
-- **社工供给不足**：社工行业迅速发展但工资低，影响就业率，很多同学做不超过一年就垮了。
-- **驻点有限**：每个街道和乡镇派两名社工驻点，主要服务老人小孩，但很难走下来。
-- **项目不稳定**：社工服务需花钱购买，今年做留守儿童、明年做留守老人，专注力不集中；不一定今年服务明年还能服务，要看领导能否争取到项目，一年服务成效不明显，资金拨不下来项目就结束。
-- **专业欠缺**：湖南省这么大，一个街道花十来万，省里拨了钱，但很多社工并非社工专业出身，可能图周末玩玩，专业上很欠缺。
-## 留守老人（发言人5、6、7）
-- **子女外出**：村里80%年轻人都出去打工了，老人无人照看。
-- **孤独求助**：有老人因寂寞报警，称“没人亲好，到哪里去请他他把我这个狗车看他不开门”。
-- **日常劳作**：老人仍要喂鱼、喂猪、打动物，一天忙很久；有老人帮人干活换鸡蛋、100块钱。
-- **就医障碍**：有视障老人说出自己在就医上遇到的障碍。
+## 农村留守老人
+- **独居比例高**：根据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%的老人与子女同住。
+- **寂寞报警案例**：黑龙江绥滨一位独居老奶奶报警称有人敲门，民警上门调查后老奶奶承认是因独自在家太寂寞、想找人聊天才报警。
+- **去世多日才被发现**：上海一名67岁独居老人在家中去世，多日后家中溢出刺鼻气味才被邻居发现；杭州一小区同样有67岁独居老人去世数天后才被发现。
+- **年轻人外出打工**：受访老人反映“现在80%都是都提醒这个在外面做做这些事的，年轻人都卖出去了”，村中留守老人无人照料。
+- **经济困难**：受访老人提到子女外出打工后经济压力大，自己靠卖鸡蛋、养猪等维持生计，有老人提到“拿你100块钱鸡蛋”。
+- **就医困难**：有视障老人向采访者说出自己在就医上遇到的障碍。
+- **无人陪伴与慰藉**：受访老人用方言表达“没得人亲好”，生病时无人照看，请人帮忙对方不开门。
+- **娱乐方式少**：民政局受访者指出留守老人“娱乐方式少，这个就坐在一起聊聊天啊，打打牌呀”。
+## 村政府/民政局干部
+- **老龄化程度持续加深**：据公安数据，2021年当地73万多人口中17.8%为老年人，且“662年到65年那个职工档案出生的人特别多，那年去年开始退休了，所以过了几年肯定就是老龄化程度会越来越严重”。
+- **三大核心问题**：一是没有很多亲人陪伴；二是经济困难，当地经济不发达；三是子女不在身边，一旦生病住院比较麻烦。
+- **养老设施运营经费无着落**：之前探索过在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但“不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的”。
+- **五保户供养标准**：集中供养的五保户自愿到敬老院，生活护理补贴直接发给敬老院护理人员；分散供养的五保户每月发475元生活费，另有护理补贴。
+- **残疾人低保标准**：一级二级残疾人纳入最低生活保障，按家庭状况分160、270、380元三档标准。
+- **农村养老金偏低**：60岁以上农村老年人每月养老金118元，受访干部指出“农村的养老金跟工人的养老金待遇完全一样，但现在的老年人公平”——意指农村老人过去交过多种税费，养老金待遇却与工人不同。
+- **基层走访力量有限**：靠村支两委和志愿者“敲门敲到那去串串门宣传政策”，每月开一次党员组织会，下午搞活动或大扫除，到孤寡老人、留守老人家里走一圈。
+- **建议方向**：请专业人员陪伴、倡导在外务工子女多联系老人、丰富文化生活、由老年协会专项执行并建固定养老设施，且“不管考虑这个建设，还要考虑后续的持续运营”。
+## 城市社区/社工
+- **城市留守老人社交机会更少**：采访者指出城市小区中的留守老人与外界社交机会更少，更容易产生孤独、抑郁等情绪。
+- **志愿者一对一帮扶**：社区建立志愿者制度，按就近帮扶原则划分一对一帮扶对象，例如志愿者发现老人住在自家楼下，就天天去看望，老人身体不好时天天送菜。
+- **志愿者激励措施**：定期表彰、志愿者积分兑换，年底可在雷锋超市兑换礼品，以维持志愿者长期坚持。
+- **“小手拉大手”活动**：今年从儿童青少年入手，让孩子拉动家长加入志愿者队伍；本周四将开展送春联活动，邀请书法老师写对联，由孩子们上门送给老人家。
+- **社区活动增进归属感**：去年中秋节开展做月饼活动，还做过百家宴，“让大家能够感觉到社区就是一个大家庭”。
+- **2023年目标**：由家长自己组织活动，社区转为协助者角色。
+- **养老服务中心**：每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务。
+- **心理问题老人案例**：一位老人因与邻里关系不和谐、半夜摔门等出现严重心理问题，志愿者上门帮扶但老人抗拒，“我不需要你的关心”，觉得周围人都是陌生的、没有关心他的人；经社工日复一日关心照料，老人心理问题逐渐好转，现在与邻里关系还算好、能接受意见，还主动给社工打电话说“寂寞空虚，得不到人关注一样”。
+- **社工供给不足**：每个街道和乡镇派两名社工驻点，主要服务老人和小孩，“但是可能说实在话也很难能够走下来”。
+- **社工工资低、流失严重**：社工行业迅速发展但工资较低，影响就业率，“基本上很多同学就没做多久，基本上都垮了，可能不超过一年”。
+- **项目资金不稳定**：社工服务领域多、专注力分散，项目需花钱购买服务，“不一定能够今年服务了，明年又能服务”，要看领导能否争取到项目；资金拨不下来、项目结束但服务成效不一定达到。
+- **社工专业性欠缺**：很多社工并非社工专业出身，“可能也就是图一个，周末玩玩”，“在专业上其实还是很欠缺的”。
 # 关键洞察与建议
-- **洞察一（数据支撑）**：2021年社区居家养老报告显示，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住；村政府干部从公安了解的数据是2021年农村60岁以上老人约73万、占17.8%，并预计因1962至1965年职工档案出生人口集中退休，老龄化程度会进一步加重。据此判断，留守老人规模庞大且呈上升趋势，养老服务的需求缺口将持续扩大。
-- **洞察二（案例支撑）**：黑龙江绥滨独居老人因寂寞报警求聊天、上海与杭州各有一名67岁独居老人去世多日后才被发现，均印证独居老人存在无人照料、无人慰藉、意外风险高发等现实困境。据此判断，独居老人的心理孤独与安全监护是当前最突出的服务盲点。
-- **洞察三（政策现状）**：村政府干部介绍，五保户分散供养每月生活费475元，另有护理补贴；民政局干部补充，五保户每月含食补电补共600来块钱，基本能满足农村生活但无余裕，残疾人一级二级纳入最低生活保障，标准分160、270、380元三档；农村60岁以上老人每月养老金118元，与工人养老金待遇不同。据此判断，现有保障标准仅能维持基本生存，难以覆盖医疗、照护等额外支出。
-- **洞察四（设施运营困境）**：村政府干部提到，此前探索在农村建养老公共设施提供日托和休闲娱乐平台，但地方财政困难，运营经费后续无支持，设施难以持续发挥作用。据此判断，养老设施建设不能只考虑一次性投入，后续运营经费的可持续性才是关键瓶颈。
-- **洞察五（社工供给不足）**：社区社工介绍，社工行业工资低影响就业率，很多同学做不超过一年就转行；湖南省每个街道派两名社工驻点，服务需花钱购买，项目不一定持续，今年服务了明年不一定能继续；很多社工并非专业出身，专业上很欠缺。据此判断，低薪酬与项目制的不稳定性共同导致社工人才流失，制约服务成效的积累。
-- **洞察六（社区活动成效）**：社区通过志愿者一对一帮扶、积分兑换礼品（雷锋超市）、小手拉大手、送春联、做月饼、百家宴等活动促进老人融入社区，2023年目标是让家长自己组织活动、社区转为协助者。据此判断，以活动为载体、以家庭带动参与的路径能有效增强社区凝聚力，且正向居民自主运营过渡。
-- **洞察七（心理干预个案）**：社区社工曾帮助一位存在心理问题的老人，该老人与邻里关系不和谐、半夜摔门、抗拒上门关心，经日复一日照料后心理问题逐渐好转，现已能接受建议并与邻里关系改善。据此判断，对心理封闭的独居老人，单纯上门探访不够，需要持续、耐心的专业陪伴才能建立信任。
-- **建议一（村政府干部提出）**：请专业施工人进行陪伴；倡导在外务工子女多与老人联系；丰富老人文化生活、增加娱乐方式；由老年协会专项执行、专门建养老设施，提供固定场地，定期开展板报宣传或健康知识讲座，并保障持续运营经费。
-- **建议二（民政局干部提出）**：依靠村支两委和志愿者，每月利用党员组织会后的时间到孤寡老人、留守老人家中串门、宣传政策、搞卫生，尽量多做上门服务。
-- **建议三（社区社工提出）**：在原有志愿者基础上发掘偏中年志愿者，并从儿童青少年入手开展小手拉大手活动，让孩子带动家长加入志愿服务；社区活动从社区策划开展转向由家长自己组织、社区作为协助者。</t>
+- **留守老人规模与风险**：2021年报告显示65.5%老人子女长期不在身边、无奈独居，仅26.8%与子女同住；黑龙江绥滨独居老人因寂寞报警求聊天，上海、杭州各一名67岁独居老人去世多日后才被发现——独居老人无人照护、意外难以及时发现是普遍风险。
+- **农村留守成因**：受访老人反映农村80%年轻人外出打工，子女经济压力大、老人适应能力降低、城市对农村老人存在无形歧视多重叠加——留守老人群体因此愈发庞大。
+- **农村养老经济困难**：民政局干部指出当地经济不发达，老人面临经济困难、子女不在身边、生病住院麻烦、娱乐方式少四类问题；分散供养五保户每月475元生活费加护理补贴，残疾人一二级低保分160/270/380元三档，农村老人每月养老金118元且与工人养老金待遇不同——现有保障水平仅够基本生活，大病或改善性需求难以覆盖。
+- **农村养老设施运营断档**：此前探索过农村养老公共设施（日托、休闲娱乐、沟通交友场地），但地方财政困难，运营经费后续无支持——一次性建设投入后缺乏持续运营资金，设施难以发挥作用。
+- **农村养老改进建议**：民政局干部提出四点建议——请专业施工人员进行陪伴、倡导在外务工子女多联系老人、丰富文化生活增加娱乐方式、希望老年协会专项执行并专门建养老设施（含固定场地、定期宣传板报和健康知识讲座），且须考虑持续运营经费。
+- **城市社区志愿者帮扶机制**：社区建立志愿者制度，一对一帮扶（如志愿者发现老人住楼下就天天去看、送菜），通过定期表彰和积分兑换（年底可在雷锋超市兑换礼品）维持志愿者积极性——就近帮扶降低老人孤独风险，激励机制保障长期坚持。
+- **志愿者队伍拓展**：社区在原有志愿者基础上发掘偏中年志愿者，今年开展“小手拉大手”活动从儿童青少年入手拉动家长加入；2023年目标转为家长自己组织活动、社区作为协助者——从“社区策划”转向“居民自组织”以增强可持续性。
+- **社区活动促进融入**：社区开展送春联（本周四，邀请书法老师写对联、孩子上门送）、中秋节做月饼、百家宴等活动，让老人感受社区大家庭氛围——活动连接孩子、家长与留守老人，传承尊老爱幼传统。
+- **养老服务中心功能**：每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务——满足老人健康维护与精神文化需求。
+- **心理问题老人个案**：社工帮助过一位与邻里关系不和谐、半夜摔门、抗拒外界关心的老人，通过日复一日上门关心和照料，老人心理问题逐渐好转，如今能接受意见、与邻里关系改善——心理问题老人需要持续陪伴而非一次性上门，社工长期关怀能带来实质转变。
+- **社工制度供给不足**：社工分为社区社工（小区出资）和街道社工（政府出资），每个街道和乡镇派两名社工驻点，但社会需求量大而供给不足，政府和社区资金有限难以承担长期专业服务费用——需求与供给严重失衡。
+- **社工流失与专业欠缺**：社工工资低影响就业率，很多同学做不超过一年就转行；不少社工并非专业出身，专业能力欠缺；项目按年度购买服务（如今年做留守儿童、明年做留守老人），资金拨不下来项目即结束，一年服务成效不明显——低薪与项目制导致人才流失、服务连续性差，阻碍行业长期发展。</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>44.1</v>
+        <v>53.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5309/3342</t>
+          <t>5309/3767</t>
         </is>
       </c>
     </row>
@@ -7904,85 +7800,85 @@
       <c r="C22" t="inlineStr">
         <is>
           <t># 沟通概况
-班主任林瑞在372班家长会上，围绕班级基本情况、教师团队、存在问题及解决思路、给家长的建议等板块与家长沟通。班级共60人，男生25人、女生35人；教师团队多数为老教师，班主任林瑞教地理学科。会上重点指出学生存在手机管理、自习效率低、书写不佳、个别学生有网瘾及早恋倾向等问题，并提出加强思想教育、制定详细班规、严格请假制度、定期与家长沟通等措施。家长代表张宇波分享家庭教育经验，强调关注孩子身心健康、尊重孩子、多倾听多交流。会议还成立家长委员会（至少三人，已有家长自愿报名），并说明保险（约310多元）、电子学生证（套餐78元）、高中资助政策（补助打在医保卡上）等事项。
+班主任林瑞在372班家长会上，面向全体家长介绍班级基本情况、教师团队、存在问题及解决思路，并说明保险、电子学生证、资助等事项；家长代表张宇波（372班大班语文老师）分享家庭教育经验。班级共60人，男生25人、女生35人；教师团队以老教师和优秀教师为主，班主任林瑞任教地理学科。会议围绕加强手机管理、严格班规班纪、关注学生心理健康与安全、成立家长委员会等议题展开，基调为家校协同、共同促进学生成长。
 # 沟通内容
-- **亮点**：班级整体时间观念与执行力较强，班风班貌纪律良好，卫生状况干净整洁；多数学生能主动向老师请教问题，对老师汇报班级情况较为积极。
-- **亮点**：学生书写整体不错，可从学生手册及抽屉中的作业本查看学习与作业情况。
-- **需关注**：个别学生书写较差，班主任已与相关家长沟通，建议家长购买字帖督促孩子练字；有学生将班号“372班”误写成“172班”。
-- **需关注**：少数同学周末沉迷手机游戏，玩累后上课状态懒散、精神不佳，约有两三个学生存在手机依赖问题。
-- **需关注**：自习课效率较低，班主任在场时学生表现安静，不在场时纪律混乱；计划加强班委培训，并安排自习课最后10分钟供学生讨论提问。
-- **需关注**：手机管理方面，要求学生在校上交手机至贴有姓名的手机存放箱；家长可不定时拨打学生电话检查是否上交，若电话能打通或无人接听则说明未交；建议家长处理家中多余手机，避免学生私藏备用机。
-- **需关注**：发现少数男生有网瘾，有学生向游戏充值400元；有男生周末外出过生日，喝酒、抽烟并观看不健康直播内容，班主任提醒家长关注手机使用内容。
-- **需关注**：发现学生带镜子进校，约10人左右，班主任要求全部收掉，并提醒家长检查孩子书包。
-- **需关注**：关注学生早恋问题，建议家长关注孩子QQ、抖音、快手等社交账号，注意是否被屏蔽，留意其朋友圈及多个账号动态。
-- **需关注**：个别学生思考能力较差，尤其在自习课上表现明显；班主任计划加强人员管理与班委培训，增强纪律意识和团队意识。
-- **需关注**：有学生生活费使用不合理，存在超支或谎称没钱的情况；班主任建议家长控制生活费额度，一般每周不超过150元（早餐约5元、午餐8元、晚餐8元，共21元/天）。
-- **需关注**：有学生周末住校期间违反纪律，外出喝酒、抽烟、玩手机；班主任强调住校生周六也须遵守宿舍纪律要求。
-- **需关注**：班主任提醒家长关注学生心理健康，发现异常及时进行心理辅导；建议家长多与孩子沟通，了解心理动态，适当给予压力，多鼓励少批评。
+**亮点**：
+- **班风班貌**：整体来看，班级时间观念和执行力强，班风班貌纪律良好，教室地面干净、卫生状况好。
+- **学习主动性**：学生遇到问题会积极上来问老师，班主任林瑞表示“他们遇到问题了，他们会积极的上来问”。
+- **师生互动**：学生非常关注老师，会主动向老师汇报情况，班主任林瑞提到“他们也会非常关注，都会主动问老师”。
+**需关注之处**：
+- **书写问题**：个别学生书写差，班主任已与家长沟通，建议家长给孩子买字帖练字；有学生把“372班”写成“172班”，字迹难以辨认。
+- **自习课纪律**：自习课效率低，班主任在场时学生表现乖，不在场时“乱哄哄的”；计划加强班委培训，并给学生10分钟讨论时间，不懂的可离开座位去问。
+- **手机管理**：发现学生玩手机，要求手机放入贴好名字的手机箱；有学生有两个手机，家长需处理多余手机；有少数男生有网瘾，曾发现学生充值400元玩游戏；有学生看直播、不健康内容，需家长管理手机。
+- **带镜子**：昨天在抽屉里发现学生带镜子，约10人，要求全部收掉。
+- **社交动态**：有学生谈恋爱，建议家长关注孩子的QQ、抖音、快手等社交账号，注意是否被屏蔽。
+- **生活费使用**：有学生生活费偏高（如400元），可能用于买手机、玩游戏或非正常消费；班主任建议家长控制零花钱，并提醒学生合理安排饮食。
+- **安全意识**：提醒未满16周岁骑电动车危险，不要载人；注意运动安全、饮食安全、防诈骗、防溺水、防校园欺凌，有事第一时间联系班主任。
+- **心理状态**：学生处于生理心理持续变化的“不稳定时期”，班主任建议家长多关注心理动态，发现异常及时心理辅导。
 # 家长反馈
-- **家长代表分享**：张宇波（校长代表、372班语文老师）以家长身份分享家庭教育经验，强调家长要控制孩子的身体健康和心理健康，做人比成绩重要，对待孩子要有平常心，尊重孩子，多倾听多交流。
-  - 张宇波提到自己作为家长感到不安，觉得没有主动参与孩子的成长，但每个孩子都有自己的个性特点，没有适合所有人的教育方法。
-  - 张宇波分享与儿子的对话，儿子问“妈妈你怎么批评我有钱”，她回答“无论怎样，那你都是爸爸妈妈心里最优秀的儿子”，认为先批评后肯定效果更深刻。
-  - 张宇波建议家长多倾听、多交流，帮助孩子重新定位，放下眼前，向往更远的风景，成为身心健康的人。
-  - 班主任林瑞提醒家长注意孩子手机使用情况，建议家长不定时打电话检查手机是否上交，并关注孩子是否有多个手机。
-  - 林瑞建议家长关注孩子的QQ、抖音、快手等社交账号，留意是否有早恋迹象。
-  - 林瑞提醒家长注意孩子生活费使用情况，建议合理控制生活费，避免孩子用于非正常消费。
-  - 林瑞提醒家长关注孩子心理健康，发现异常及时进行心理辅导。
-  - 林瑞提醒家长注意交通安全，未满16周岁骑电动车非常危险，尤其不能载人。
-  - 林瑞提醒家长注意防诈骗、防溺水、防校园欺凌，遇到问题第一时间联系班主任。
-  - 林瑞建议家长为孩子创造良好的家庭环境，避免当着孩子面长时间玩手机，不在家里聚众打麻将。
-  - 林瑞建议家长多鼓励少批评，给孩子制定容易达到的小目标，激发潜能。
-  &gt; “做人的话是我们的必修技能。要想让孩子离开，就要让他们学会怎么样做人，千万不能让他们带上不良的风气。”
-  &gt; “家长对待孩子，就是要有一个平常心，孩子们面临的学习压力很大，对于挫折和失败，那也可以做卖货。”
-  &gt; “要尊重孩子，如果一个人从小就能得到大人的尊重，长大后他肯定也会尊重别人。要给孩子一个自由空间，不要轻易给孩子下消极的评价。”
-  &gt; “多倾听，多交流，多与我们孩子之间对工作进行孩子的教育。特别的特别的烦恼，然后还有真正的就是他们的一些事件。”
-  &gt; “无论怎样，那你都是爸爸妈妈心里最优秀的儿子，你先批评他，还是不当，这样的话他会更加的深刻。”
+- **家长代表张宇波**：作为372班大班语文老师，分享家庭教育经验，强调家庭要控制孩子的身体健康和心理健康，做人是必修技能，要先做人。
+- **家长代表张宇波**：主张家长要有平常心，孩子学习压力大，要帮助孩子面对挫折和失败，重新给自己定位，放下眼前，向往更远的风景。
+- **家长代表张宇波**：强调要尊重孩子，给孩子自由空间，不要轻易给孩子下消极评价，不要以夸儿自豪，要尊重孩子心理上追求尊重与要求。
+- **家长代表张宇波**：建议多倾听、多交流，给予孩子更多关爱与理解，帮助孩子以更好的状态面对学习。
+- **家长代表张宇波**：分享与儿子的对话，儿子问“妈妈你怎么批评我有钱”，她回应“无论怎样，那你都是爸爸妈妈心里最优秀的儿子”，认为先批评不当，这样孩子印象更深刻。
+- **家长代表张宇波**：强调要遵守学校制度、配合老师工作，做一个有质量的老师。
+&gt; 我首先给他的就是安慰他，他因为不敢写怎么样，主要是你过去的。
+&gt; 我说无论怎样，那你都是爸爸妈妈心里最优秀的儿子，你先批评他，还是不当，这样的话他会更加的深刻。
+- **家长关注点**：孩子面临的学习压力大，需要帮助孩子面对挫折和失败。
+- **家长关注点**：孩子需要得到尊重，不应被轻易下消极评价。
+- **家长关注点**：家长要多倾听、多交流，给予孩子关爱与理解。
+- **家长关注点**：家长要遵守学校制度、配合老师工作。
 # 共识与配合事项
-**费用与收费管理**
-- [ ] **家长**：确认水费险每人每月2元，按每两周或每月收取，卫生不达标时另行补充，费用由学生交给生活委员，不在微信群转账
-- [ ] **家长**：确认书费预交11000元（已购5本书），尚未结算，待学校核算后多退少补
-- [ ] **家长**：确认未购买书箱的同学，相关费用将退还；少数同学费用约100元，无效费用约70元，具体明细由班主任后续公布
-- [ ] **家长**：警惕冒充班主任在微信群收费的诈骗行为，所有费用由学生当面交给生活委员，不在群内转账
-- [ ] **班主任**：费用明细（含书费、水费险等）核算完成后，通过电话或群通知家长，不通过微信群收取任何费用
-**保险与电子学生证**
-- [ ] **家长**：确认学生保险费用约310多元，可自行选择购买渠道（学校、保险公司、线上平台均可），购买后需告知班主任以便统计
-- [ ] **班主任**：统计全班学生保险购买情况，确保每位学生都有保障
-- [ ] **家长**：确认电子学生证套餐78元（移动可办），用于方便联系和请假；班级现有3个座席，其中2个已到期（9月20几号到期），1个可用，班主任将把新号码发到群里供家长补充
-- [ ] **家长**：确认电子学生证办理自愿，能办则办，不能办可说明情况；具体业务可自行咨询相关公司
-**资助政策与住校纪律**
-- [ ] **家长**：确认高中资助政策与初中不同，所有补助（含营养餐、生活补助）直接打在学生医保卡上，不再发到卡上；每次打钱班主任会通知家长，家长需关注孩子如何使用补助金
-- [ ] **家长**：确认住校生周六留校须遵守宿舍纪律，午休2:10开始，不得外出喝酒、抽烟、玩手机
-- [ ] **班主任**：将资助政策文件发到家长群，供家长查阅；每次补助发放时通知家长，提醒家长关注资金用途
-**手机与网络管理**
-- [ ] **家长**：配合学校管理孩子手机，周一到周五不定时打电话检查手机是否上交（打过去无人接听说明已交）；家中多余的手机（含备用机、旧手机）应收掉或处理，避免孩子藏匿
-- [ ] **家长**：关注孩子手机使用内容，检查是否安装游戏、直播、不健康应用；关注孩子QQ、抖音、快手等社交账号，留意是否有早恋迹象或被屏蔽
-- [ ] **家长**：发现孩子有网瘾（如周末充值游戏400元等）及时干预，控制生活费额度（建议每周不超过150元，按早餐5元、午餐8元、晚餐8元标准）
-- [ ] **班主任**：班级设手机存放箱，每位学生名字贴好，上课期间统一上交手机
-**安全与行为规范**
-- [ ] **家长**：提醒孩子注意交通安全，未满16周岁不得骑电动车，尤其不得载人；如确需骑行须单人骑行并遵守交规
-- [ ] **家长**：配合学校做好防诈骗、防溺水、防校园欺凌教育；孩子在校遇到问题（如被欺凌、矛盾冲突）第一时间联系班主任处理
-- [ ] **家长**：关注孩子心理健康，发现异常及时与班主任沟通，必要时进行心理辅导
-- [ ] **家长**：提醒孩子注意运动安全、饮食安全，合理安排饮食、补充营养
-- [ ] **班主任**：对校园欺凌等事件第一时间介入处理（如曾有学生11点发生矛盾，班主任12点约谈至2点）
-**学习与习惯培养**
-- [ ] **家长**：查看学生手册中孩子的书写情况，书写不好的孩子请购买字帖练习（如文具店有售）
-- [ ] **家长**：关注孩子自习课效率，配合班主任加强班委培训，培养纪律意识和团队意识
-- [ ] **家长**：与孩子共同制定月考目标（下次月考在11月初），目标要适当、可达成，避免过高或过低
-- [ ] **家长**：多鼓励、少批评，关注孩子心理动态，给孩子适当压力但不过分期望
-- [ ] **班主任**：继续加强思想教育工作，制定详细班规（扣分、写检讨、罚站等），严格请假制度，定期与家长沟通学生在校表现
-**家校协作**
-- [ ] **家长**：自愿报名参加家长委员会（至少3人，已有家长报名），与班主任、学校共同促进学生成长
-- [ ] **家长**：为孩子创造和睦、祥和的家庭氛围，不在孩子面前长时间玩手机、不聚众打麻将、不常备零食，避免过多唠叨
-- [ ] **家长**：多抽时间了解孩子在校表现，经常给孩子制定容易达成的小目标（如年级排名进步），激发潜能
-- [ ] **班主任**：将各科教师联系方式发到家长群，方便家长联系；家长会后续安排（下午3:20-3:25可办理相关事项，3:30有培训）</t>
+**家校共识**
+- **共识**：孩子成长30%靠自身，70%需家校配合支持；班主任林瑞与家长代表张宇波均强调关注学生身心健康、尊重孩子、多倾听多交流、配合学校制度。
+- **共识**：班级管理以严格班规班纪、稳定学习秩序为原则，班主任将定期与家长沟通学生表现。
+- **共识**：手机管理需家校联动，家长负责处理多余手机，班主任负责在校统一收纳与监督。
+**班主任待办**
+- [ ] **班主任**：制定并执行详细班规，每项违规按规扣分、写检讨、罚站，严格请假制度。
+- [ ] **班主任**：每天开展思想教育工作，加强班委培训，提升自习课纪律与效率。
+- [ ] **班主任**：在教室设置手机收纳箱，每个学生名字贴好，统一收存手机。
+- [ ] **班主任**：收掉学生携带的镜子（约10人），并持续检查书包等物品。
+- [ ] **班主任**：定期与家长沟通学生课堂表现、作业情况及心理动态。
+- [ ] **班主任**：统计学生保险购买情况，汇总后跟进未购买学生。
+- [ ] **班主任**：将新的电子学生证号码发到家长群，供家长补充更新。
+- [ ] **班主任**：将资助政策文件发至家长群，并逐次告知补助发放金额与时间。
+- [ ] **班主任**：组织家长委员会后续会议，与家委会共同探讨班级重要事项。
+- [ ] **班主任**：关注学生社交动态（QQ、抖音、快手等），发现异常及时与家长沟通。
+- [ ] **班主任**：对心理异常学生及时进行心理辅导，必要时联系家长。
+- [ ] **班主任**：处理校园欺凌等突发事件，学生有事第一时间介入处理。
+**家长待办**
+- [ ] **家长**：处理学生多余手机，只保留一部可用手机，其余收走或销毁。
+- [ ] **家长**：周一到周五不定时拨打学生电话，验证手机是否在校、是否开机。
+- [ ] **家长**：检查学生书包及随身物品，配合收掉镜子等违禁品。
+- [ ] **家长**：关注学生QQ、抖音、快手等社交账号，留意是否被屏蔽及恋爱迹象。
+- [ ] **家长**：对书写差的学生，到文具店购买字帖，督促每日练字。
+- [ ] **家长**：控制学生零花钱，建议每周不超过150元（早餐约5元、午餐8元、晚餐8元），防止非正常消费。
+- [ ] **家长**：提醒学生注意交通安全，未满16周岁不得骑电动车，更不得载人。
+- [ ] **家长**：提醒学生注意运动安全、饮食安全、防诈骗、防溺水。
+- [ ] **家长**：发现学生异常情况（如被欺凌、心理波动）第一时间联系班主任。
+- [ ] **家长**：为学生购买保险（约310多元），可在学校、菜市场或线上平台自行购买，购买后告知班主任统计。
+- [ ] **家长**：办理电子学生证（移动套餐满78元可办），方便联系学生；无法办理的向班主任说明。
+- [ ] **家长**：关注资助政策，高中补助打在学生医保卡上，每次到账后与班主任确认金额及用途，防止学生乱花。
+- [ ] **家长**：自愿报名参加家长委员会（至少3人），参与班级重要事项探讨。
+- [ ] **家长**：创造和睦家庭环境，避免在孩子面前长时间玩手机、唠叨、聚众打麻将。
+- [ ] **家长**：多与孩子沟通，了解心理动态，适当给压力、多鼓励少批评，不与其他孩子比较成绩。
+- [ ] **家长**：与孩子共同制定容易达到的小目标（如年级排名进步），激发潜能。
+- [ ] **家长**：提醒住校学生遵守宿舍纪律，周六住校同样遵守就寝规则，不得饮酒、吸烟。
+- [ ] **家长**：关注补助资金使用，防止学生用于买手机、过生日请客、喝酒唱歌等非学习消费。
+**费用与收费说明**
+- **费用**：书费已预交11000元，目前购买5本书，尚未结算，后续多退少补。
+- **费用**：部分学生未购买外部书箱，相关费用将退还。
+- **费用**：少数学生费用约100元左右，其中无效费用约70元；班费标准为每月2元/人。
+- **费用**：班主任明确不在微信群收取任何费用，需交费用由学生直接交给生活委员，防止诈骗。
+- **费用**：提醒家长防范冒充班主任头像在群内收费的诈骗行为，涉及转账务必电话核实。</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>58.9</v>
+        <v>67</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17334/4000</t>
+          <t>17334/3321</t>
         </is>
       </c>
     </row>
@@ -8063,58 +7959,44 @@
       <c r="C23" t="inlineStr">
         <is>
           <t># 例会概况
-本次周会于10月28日召开，会议等级为自愿级，主题为总结工作，目标是初步统一成员意见、统一对社区的认识。会议资料包括工作报告、这班看法、这班型社区介绍。会上围绕工作方向、任务安排、社区宣传、待遇休假及下周工作等议题展开讨论。
-工作方向方面，计划建设教育办的师范学校，第三步参加互联网加创业大赛，第四步根据学校为学府学习所需技能，实现一定范围内的教师改革。目前共有四个任务，包括课程开发，下月主要任务为组建执法队伍。任务一第一步为确定路线、修订纲领章程，修订303相关文件已基本完成。
-社区介绍文件已修改，将“我们是谁”提到最上面，并讨论了抖音任务、公众号宣传及可视化学习方案和工具。待遇方面，上班5000元，额外有奖励和提成，休假为周五半天加周末两天。下周工作包括邀请同事加入、完成两个活动、组建教育团队，并需提交符合要求的政府报告。
-会上指出全场活动的优美和棒棒糖待遇尚未发放，影响入职，需发放完成后方可入职。任务分配中菜品条件可能不同。会议纲要是否还需修改、是否要报上上等问题尚未明确。
+本次周会于10月28号周召开，主题为总结工作，会议等级为自愿级，由主持人发言人1主持。会议资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。会议围绕工作方向与任务安排、社区介绍与宣传、任务分配与执行、待遇与休假等议题展开讨论，其中工作方向与任务安排、社区介绍与宣传、待遇与休假均处于讨论与同步阶段，任务分配与执行已明确下月主要任务为组建执法队伍。整体来看，社区介绍文件已完成修改，将“我们是谁”提到最上面，推进较为顺利；但工作量可能偏大，部分活动重要性不高，需成员互相理解。会议明确需组建教育团队、确定路线并修订纲领章程，待遇为上班5000元、额外有奖励和提成，休假为周五半天加周末两天；会议纲要是否修改、是否报上上等事项仍待定。关键数字与节点：目前共4项任务，下月主要任务为组建执法队伍，需招聘20多位师傅。
 # 工作进展
-## 工作方向与整体任务
-- **教育办师范学校建设**：计划建设教育办的师范学校，第三步参加互联网加创业大赛，第四步根据学校为学府学习所需技能，实现一定范围内的教师改革；下一步按步骤推进，时间节点未明确。
-- **社区服务定价模式**：希望将服务定价权交给消费者，因此将服务转变为代购模式；下一步继续完善该模式设计。
-- **工作方法改进**：公司以前用传统方法，现在用AI后效率提高、质量改善；下一步在实践中继续探索改进。
-## 当前四项任务
-- **课程开发**：为当前四个任务之一，需完成课程开发工作；下一步按任务分配推进，时间节点未明确。
-- **组建执法队伍**：为下月主要任务，占比最大，需招聘20多位师傅组建教育班队，人数尽量控制规模；下一步确定路线、修订纲领章程后安排任务分配。
-- **大运发放**：需要调试，工作刚开始，目前仅为志愿者阶段；下一步继续调试推进。
-- **活动页面设计**：明日边缘分享活动页面，需统计费用；下一步确认预算与设计方案。
-## 任务一：确定路线与修订纲领章程
-- **确定路线**：任务一第一步为确定路线，修订纲领章程；下一步按此推进。
-- **修订303相关文件**：已修订差不多，基本完成；下一步请成员自行查看并打勾确认。
-- **纲领章程修订**：已修订完成，基本接近尾声；下一步安排任务分配，有意愿运行者可安排任务。
-## 社区介绍与宣传
-- **社区介绍文件修改**：已将“我们是谁”提到最上面，修改完成；下一步继续完善介绍内容。
-- **抖音任务**：讨论抖音宣传任务，涉及可视化学习方案和工具；下一步确定宣传方案与费用。
-- **公众号宣传**：讨论公众号宣传方式，需留下公众号信息；下一步完善公众号运营。
-- **社区介绍修改参数**：已根据修改的参数更新文件；下一步继续优化。
-## 待遇与休假
-- **薪资待遇**：上班5000元，额外有奖励和提成；下一步月会上再发薪资待遇。
-- **休假安排**：周五半天加周末两天休假；下一步按此执行。
-## 下周工作安排
-- **邀请同事加入**：下一步邀请同事加入，会后看有谁愿意参与；时间节点为会后。
-- **完成两个活动**：需完成两个活动，活动不是特别重要但需互相理解；下一步安排活动执行。
-- **组建教育团队**：需要组建教育团队；下一步推进组建工作。
-- **政府报告**：仍需政府报告，要符合要求；下一步按标准提交。
-## 待发放与阻塞事项
-- **活动待遇发放**：全场活动的优美和棒棒糖待遇尚未发放，今天统计出来，发放完成才能入职；下一步发放后办理入职，时间节点未明确。
-- **任务分配差异**：任务分配中菜品条件可能不同；下一步根据实际情况调整。
+## 工作进展
+### 社区介绍与宣传
+- **社区介绍文件修改**：已将“我们是谁”部分提到文件最前面，并调整了两个镜头的衔接；下一步继续完善介绍内容，供成员审阅确认。
+- **宣传渠道规划**：讨论了抖音任务与公众号运营，提出可视化学习方案和工具；下一步确定各渠道发布节奏与内容分工。
+- **宣传物料设计**：封面已发送给成员查看，社区介绍文件整体风格需进一步优化，使其更美观、气质更佳。
+### 任务规划与执行
+- **课程开发**：为当前四个任务之一，需按学校需求学习所需技能，并实现一定范围内的教师改革；下一步明确课程内容框架与开发分工。
+- **组建执法队伍**：为下个月主要任务，需招聘**20多位师傅**，组建教育班队；任务一第一步为确定路线、修订纲领章程，该部分已修订完成，待成员自行查看并确认。
+- **大运发放**：需要调试相关流程，目前工作刚开始，负责人为志愿者身份；下一步完成调试并安排发放。
+- **活动安排**：需完成两个活动，其中一个为“明日边缘”分享活动，需统计活动页面费用；活动重要性一般，但需成员互相理解配合。
+- **参加互联网加创业大赛**：列入工作方向，需进一步规划参赛方案与团队分工。
+### 待遇与休假
+- **薪资待遇**：上班**5000元**，额外有奖励和提成；具体薪资方案留待月会再行发布。
+- **休假安排**：周五半天加周末两天；需按此标准安排人员排班与任务时间。
+### 其他工作事项
+- **账单统计**：今日余额趋势较上次增多，因有两个账单尚未发送（全场活动的优美和棒棒糖待遇未发放）；需先完成发放再办理入职。
+- **社区环境建设**：需具备政府资源，社区环境对成员学习有重要影响；下一步联系官方对接资源。
+- **章程修订**：已参照党章修改情况（原坚持四项基本原则改为五项）进行修订，修订工作已基本完成，待成员确认。
 # 协作需求
-- **邀请同事加入**：发言人1提出下一步邀请同事加入，以共同制作解决方案，需成员配合参与；未明确具体时间节点。
-- **组建教育团队**：发言人1提出需要组建教育团队，需成员配合参与组建；未明确具体分工与时间。
-- **完成两个活动**：发言人1安排需完成两个活动，虽说明活动不是特别重要，但需成员互相理解并配合完成；未明确活动内容与截止时间。
-- **提交政府报告**：发言人1提出仍需政府报告，需成员配合准备材料，且要符合要求；未明确具体提交时间。
-- **修订纲领章程**：发言人1指出任务一第一步为确定路线、修订纲领章程，需成员配合查看已修订的303相关文件并确认；未明确确认截止时间。
-- **任务分配确认**：发言人1提出任务分配需确认，因菜品条件可能不同，需成员配合反馈各自条件；未明确反馈时间。
-- **活动页面费用统计**：发言人1询问活动页面总花费，需成员配合统计剩余费用；未明确统计完成时间。
-- **会议纲要修改**：发言人1询问会议纲要是否还需修改，需成员配合提出修改意见；未明确修改截止时间。
-- **是否报上上**：发言人1提出是否报上上需讨论，需成员配合参与讨论并给出意见；未明确讨论时间。</t>
+- **邀请同事加入**：发言人1提出下一步邀请同事加入，共同制作解决方案，会后将看有谁愿意参与；需相关成员配合确认参与意向。
+- **任务分配与认领**：发言人1要求成员查看已修订的纲领章程等文件并自行确认，用打勾方式反馈完成情况；需各成员在会后完成确认。
+- **任务优先级调整**：发言人1指出某任务优先级安排不当，要求张经理将下周洛阳行程相关事项排到第二项，并修改任务安排。
+- **活动执行配合**：发言人1提到需完成两个活动，虽非特别重要但需大家互相理解并配合执行。
+- **课程开发协作**：课程开发任务需相关成员配合推进，具体分工待任务分配后明确。
+- **执法队伍组建**：下月主要任务为组建执法队伍，需招聘20多位师傅，需相关成员配合招聘与组建工作。
+- **大运发放调试**：大运发放任务需要调试，相关负责成员需配合完成调试工作。
+- **社区介绍修改确认**：社区介绍文件已修改并将“我们是谁”提到最上面，需成员查看确认修改效果。
+- **宣传方式配合**：抖音任务、公众号宣传及可视化学习方案和工具需相关成员配合推进。</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>36.4</v>
+        <v>34.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4999/2139</t>
+          <t>4999/1669</t>
         </is>
       </c>
     </row>
@@ -8571,38 +8453,39 @@
       <c r="C24" t="inlineStr">
         <is>
           <t># 就诊概况
-消化内科严医生于门诊接诊48岁男性患者张春和，患者为成都轻工研究所科研人员。本次就诊核心主诉为上腹反复不适3个月，近4年每年春季发作上腹烧灼感，由冷、硬、刺激性食物或工作紧张劳累诱发，白天发作、无夜间痛醒；一年前与三个月前各出现一次黑便，最近两个月出现呕吐。初步判断需进一步检查，已预约后天胃镜，并计划向上级张医生汇报。
+患者张春和，男，48岁，在成都轻工研究所从事科研工作，因上腹反复不适3个月就诊于消化内科。严医生接诊，围绕上腹烧灼痛、两次黑便及呕吐等主诉系统采集现病史、既往史、个人生活史及家族史，初步判断需进一步检查，已预约后天胃镜并建议留大便排查出血。
 # 病史与背景
-- **现病史**：上腹反复不适3个月，近4年每年春季发作，心窝处烧灼感，吃冷、硬、刺激性食物或工作紧张劳累时诱发，与油腻食物关系不大；白天发作，无夜间痛醒，疼痛可忍受，工作轻松时有完全不痛间歇。
-- **黑便**：一年前与三个月前各出现一次，每次持续约一个月，大便干、形状正常，每天最多两次；两次均住院（分别约10天、两三天）后转为黄色。
-- **呕吐**：最近两个月出现，吐出酸水样物，为早、中餐食物，晚上吐出后舒服，偶有隔夜食物吐出。
-- **近期用药**：斯达舒初时有效，后效果不佳，加量至每天四五次仍效果不好；奥美拉唑（武汉药厂产，国产）和阿莫西林，以及医务室自配胃炎合剂，停药后症状反复。
-- **既往史**：16岁患甲肝，在三医院住院一个月，出院及此后体检肝功能均正常；小时候因扁桃体炎在儿童医院就诊，服用华安药后左手起红疹持续半个月，医生诊断为药物过敏，此后不能服用该药。
-- **过敏史**：华安药过敏，服用后左手起红疹，持续半个月。
-- **家族史**：父亲76岁有低血压，患者本人也有低血压（90/60）；母亲75岁诊断冠心病，服药控制良好；有一个弟弟身体健康；婶婶（叔叔的爱人）患胃癌。
-- **个人史**：出生并长期生活在成都，在成都轻工研究所从事科研工作，工作紧张、经常加班熬夜；吸烟（以前一天一包，现限制在10支以内，考虑戒烟），偶尔饮酒，喝淡茶（每天泡两次）；眼睛近视400度，偶尔口腔溃疡，无皮肤瘀斑、牙龈出血、咳嗽咳痰、心慌心累，偶有急性腹泻。
+- **现病史**：上腹烧灼感3个月，与进食冷、硬、刺激性食物及工作紧张劳累相关，近4年每年春季多发；近3个月疼痛白天发生，无夜间痛醒，有完全不痛的时候。
+- **黑便**：近一年内两次，分别在一年前和三个月前；第一次持续约一个月并住院约10天，第二次住院两三天好转，大便干、形状基本正常。
+- **呕吐**：最近两个月出现，吐出酸水样物，含早晨或中午食物，晚上吐出后舒适，有昨晚食物今天吐出的情况。
+- **既往史**：16岁患甲肝，在三医院住院一个月，出院及后续体检肝功能均正常；小时候因扁桃体炎在儿童医院就诊。
+- **过敏史**：服用华安药后左手起红疹，持续半个月，医生诊断为药物过敏，母亲提醒不能吃该药。
+- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，仅有一个弟弟身体很好；一位婶婶患胃癌，但严医生解释婶婶无血缘关系，不必担心遗传。
+- **个人史**：出生并长期生活在成都，工作紧张、经常加班熬夜；吸烟（以前一天一包，现限制在10支以内，考虑戒烟），偶尔饮酒，喝淡茶一天泡两次；26岁结婚，有一小孩，爱人及小孩身体健康。
+- **近期用药**：斯达舒（初时有效后效果不佳，加量至每日四五次仍效果不好）、奥美拉唑（武汉药厂国产）、阿莫西林及医务室自配胃炎合剂，停药后症状反复。
 # 诊断与检查结果
-尚未给出明确诊断结论。已安排大便潜血检查以排查消化道出血，并预约后天胃镜进一步检查。
+严医生初步判断患者需进一步检查，尚未给出明确诊断结论。建议留大便排查出血，并预约后天胃镜。患者有两次黑便史，需排查消化道出血；有胃癌家族史（婶婶），虽无血缘关系，但患者担心，需进一步检查排除。
 # 治疗方案与医嘱
-- **检查安排**：留大便做潜血检查，排查消化道出血；预约后天胃镜，因患者爱人后天可请假陪同。
-- **生活方式**：建议戒烟、尽量少喝酒，因吸烟饮酒可能加重胃肠道疾病；注意避免熬夜，工作紧张劳累可能诱发症状。
-- **复诊与陪同**：后天胃镜需有爱人陪同；严医生将总结情况后向上级张医生汇报，再商定下一步处理意见。
+- **检查安排**：留大便做检查以排查出血；胃镜预约在后天进行，因患者爱人可请假陪同，且后天张大夫查房，安排较好。
+- **用药说明**：近期服用斯达舒效果不佳，加量至每日四五次仍效果不好，需进一步评估调整。
+- **生活方式**：建议戒烟、尽量少喝酒，因吸烟饮酒可能加重胃肠道疾病；注意工作紧张、经常熬夜可能诱发或加重症状。
+- **复诊与陪同**：胃镜需由爱人请假陪同；严医生将总结病情向上级张医生汇报，再商定下一步处理意见。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 斯达舒 | 未提及 | 最初一天两次，每次一颗；现加至每天四五次 | 口服 | 初时有效，后效果不佳，加量后仍效果不好 |
-| 奥美拉唑 | 未提及 | 未提及 | 口服 | 武汉药厂产，国产 |
+| 斯达舒 | 未提及 | 最初一天两次，每次一颗；后加至每日四五次 | 口服 | 初时有效，后效果不佳 |
+| 奥美拉唑 | 未提及 | 未提及 | 口服 | 武汉药厂国产 |
 | 阿莫西林 | 未提及 | 未提及 | 口服 | 未提及 |
 | 胃炎合剂 | 未提及 | 未提及 | 口服 | 医务室自配 |
 # 复诊与预警信号
-复诊时间为后天（胃镜检查日），届时张大夫查房。⚠️ 需立即就医的预警症状：出现黑便（既往有两次黑便史，需警惕消化道出血）；呕吐物带红色或黑色（原文询问但患者未确认，需警惕）。</t>
+复诊时间未明确，胃镜预约在后天进行。⚠️ 需立即就医的预警症状：原文未提及具体预警症状，但患者有两次黑便史，需警惕消化道出血。</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>56.7</v>
+        <v>49.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10297/1372</t>
+          <t>10297/1318</t>
         </is>
       </c>
     </row>
@@ -8941,94 +8824,105 @@
       <c r="C25" t="inlineStr">
         <is>
           <t># 讲座概况
-肖楠总在本次专项讨论会上向投资者汇报过去一年的研究布局、投资框架的反思与更新，并回答投资者提问。肖楠首先指出知识与信息之间存在巨大鸿沟，投资者关心的“what happen next”问题并非其研究重点，其研究框架将问题分为重要不重要、可研究及难以研究四类，重点关注标的基本面变化、投资逻辑更新、认知深入领先及投资框架修正。
-肖楠明确反对市场上流行的“抱团”和“均值回归”两种观点。他认为“抱团”定义不本质，基金经理之间是竞争关系，主观上不可能抱团；均值回归是局部正确，90%时间正确但10%错误代价惨重，并以某商学院老师在海螺水泥上做波段、2016/2017年卖出后两年涨五六倍再未买回为例说明。他强调收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。
-过去一年研究布局集中于四大方向：互联网、财富管理、新消费、高端制造。互联网领域全球仅中国和美国能做成巨大产业，中国已迭代三代企业（流量、运营、算法），港股通开通后可投；财富管理行业因中国人均收入中位数提升5%-10%将带来巨额剩余财富，行业空间远超想象；新消费公司从CEO到组织架构、经营理念与传统企业完全不同；高端制造领域中国是全球几乎唯一拥有全产业链的国家，很多领域已占据主导地位。
-肖楠分享了过去一年对投资框架的五点反思：一是商业模式分类（坐地收钱、苦尽甘来、燃烧自己照亮别人）不完备，世界上没有一劳永逸的坐地收钱生意；二是从商增角度理解商业模式更本质，企业成长靠吸收熵增；三是错过中期10倍投资机会，因终局判断悲观而放弃，但企业后来涨十几倍，刺激反思；四是长期变量（如国运、文化背景）可能解释相当部分收益率来源，需保持谦卑；五是深度价值可能长期无效（打问号），去年投的深度价值标的结果很差。此外，他提出小企业X factor概念，即驱动企业增长且不被线性描述的因子，经典模型无法定价但长期重要。
-在投资者问答环节，肖楠就中期投资机会、伟大公司判断标准、全市场基金投资逻辑、血制品行业、农林牧渔行业、商增商减分析、增长曲线、财富管理行业、企业家精神等问题作出回应。他提到因错过十几倍涨幅而反思，未来在终局判断不乐观时仍可把握中期机会；伟大公司财务指标看不出来，举例A公司（高研发、产业报国）与B公司（管理精益）对比；全市场基金选股逻辑与消费基金完全一样；血制品行业研究不多、壁垒不强、未买入；农林牧渔行业提升因牧原股份，非看好行业；商增商减用企业部门增多、效率变差等例子解释；增长曲线以顺丰疫情时脱颖而出、美的渠道改革后超越格力为例；财富管理行业分层，财富分布不均匀，头部公司可能拿走增量绝大部分；企业家精神需谨慎归因，不轻易定价，只在客观归因穷尽后考虑。
+肖楠总面向机构投资者作年度研究布局与投资框架汇报，主题为过去一年的研究布局、投资框架反思与更新，形式为专项讨论会。开场即点明投资者关心的“what happen next”问题并非其研究重点，强调知识与信息之间存在巨大鸿沟，并介绍其研究框架将问题分为重要不重要、可研究及难以研究四类。汇报围绕四大研究布局方向（互联网、财富管理行业、新消费、高端制造）与五点投资框架反思展开，核心主张包括：明确反对“抱团”与“均值回归”两个流行观点，认为收益率呈幂律分布而非正态分布；提出驱动企业增长且不被线性描述的“X factor”因子，经典模型无法定价但长期重要。关键锚点包括：美国股市200年价值增量由4%的公司贡献；某商学院老师因相信均值回归，在海螺水泥上错失两年五六倍涨幅；中国互联网产业短短十几年已迭代三代企业。对听众而言，本次汇报旨在让投资者了解基金经理的研究积累、看问题角度及投资框架的自我扬弃，以检验其认知是否持续升级。
 # 核心观点与论证
 ## 论点：知识与信息之间存在巨大鸿沟，投资者关心的“what happen next”问题并非研究重点
-- **知识鸿沟**：肖楠指出，他看好某板块或个股是基于相关知识（`knowledge`），而投资者得到的仅是一条“肖楠看好某某”的信息，两者存在巨大鸿沟；他的观点可能因新知识增加而次日改变，但投资者可能需等一年甚至更久才知道。
-- **研究框架四分类**：肖楠将问题分为重要不重要、可研究及难以研究四类；他真正关心的是标的基本面是否变化、投资逻辑有无更新、对标的认知是否更深入领先、投资框架有无值得修正之处，这些是可被研究的“富矿”。
-- **框架因人而异**：该表仅针对肖楠个人，例如基于宏观变量做资产配置的人，会认为美联储利率变化对市场的影响是既重要又可研究的问题。
-## 论点：反对“抱团”观点，认为其定义不本质
-- **定义不本质**：肖楠认为“抱团”定义不本质，会导致研究误入歧途；他以“光明使者”为例——若给一叫就出太阳的动物取名“光明使者”，会误以为宰了它太阳就不出来，同理“抱团”只是现象，不说明问题。
-- **主观上不可能**：基金经理之间是竞争关系，主观上不可能商量好一起买某只股票；肖楠举例称不可能打电话给嘉实基金王经理、富国李经理商量“抱团”，大家是竞争对手，推荐股票还可能被怀疑是“让我踩脚”。
-- **同一公司买同板块不叫抱团**：研究员推荐股票、多位基金经理认可后买入是正常运作；若这算抱团，则“研究员每推荐一个股票，抽取三位幸运基金经理去买”的做法荒谬不可行。
-- **截面数据忽略时间维度**：肖楠称其8年前、5年前就买入某些标的，后来大量资金蜂拥而至，他“一脸懵”；拉长时间看，A股和海外股市都有类似现象，如当年的“五朵金花”“眉飞色舞”“长牛的医药消费”。
-## 论点：反对“均值回归”观点，认为其是局部正确
-- **均值回归定义**：肖楠解释均值回归即“跌多了要涨，涨多了要跌”；短期看K线图确实如此，但拉长看无法解释10年涨10倍、20倍、50倍、100倍的长线牛股。
-- **海螺水泥案例**：某商学院老师过去10年在海螺水泥上做波段赚两三倍，2016或2017年卖出后等回调，结果两年内股价涨五六倍，再也没能买回；肖楠总结“均值回归90%的时间都正确，那10%的错误依然让你代价惨重”。
-- **收益率幂律分布**：肖楠强调收益率是幂律分布而非正态分布，投资核心是找到摆脱“涨多跌多”局部规律的长线超级大牛股；美国股市200年价值增量由**4%的公司**贡献，挖掉这4%的公司，200年来美国股市没有涨。
-## 论点：过去一年研究布局集中于四大方向
-- **互联网**：全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业——第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）；港股通开通后可投此前无法投的公司，不能容忍错失机会。
-- **财富管理行业**：中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，因巨大基数效应和收入分布密度效应会有巨额剩余财富，有待专业机构管理；行业增速和潜在空间“远超我们想象”。
-- **新消费**：新一代消费公司从CEO想法理念、基层执行人员、生产方式到营销方式，与匮乏年代走出来的传统企业完全不同，不是产品够新才叫新消费，而是组织架构和经营理念根本不同；随着中国越来越富裕，这类公司会越来越多。
-- **高端制造**：中国是全球几乎唯一拥有全产业链的国家；微观深入制造业细分领域可见中国已在很多领域占据主导地位，与10年前“10亿双袜子换台飞机”的理解完全不同；欧美日企业可得的市场份额“已经是中国企业碗里的肉”。
-## 论点：过去一年重要认知——新消费领域产品差异与商增视角
-- **产品差异巨大**：肖楠过去不理解有些东西为何卖得火，表面看两家公司产品差不多，但收入利润体量差距巨大；深入研究发现，产品经理团队或CEO眼中自家产品与竞争对手存在巨大鸿沟，这种差异在三年、五年、十年维度会被放得非常大。
-- **新消费行业格局**：传统消费行业龙头赚钱、龙二龙三也赚钱；新消费领域同样巨大的行业可能只有两家公司，一家赚很多钱，另一家完全不挣钱、不知怎么挣钱，差异极大。
-- **商增与商业模式**：肖楠去年产生重要想法——从商增角度理解企业商业模式；成长企业商增速度差异巨大，商增过快导致企业走向失败，研究大量失败案例后发现商增是理解商业模式的重要角度。
-## 论点：投资框架反思之一——商业模式分类不完备
-- **三类商业模式**：肖楠将生意分为三类——`坐地收钱`（最喜欢买）、`苦尽甘来`、`燃烧自己照亮别人`（不值得买）；至今仍相信这一划分，但承认框架有不完备性。
-- **没有一劳永逸的生意**：世界上没有一劳永逸的坐地收钱生意，极端稀缺；哪怕爱马仕，一个设计师的好坏也可能影响未来五年十年销售；长期看所有企业都要死去，单一维度出发会错失很多机会。
-- **商增更本质**：有些企业从诞生到收入和利润涨100倍，结构没特别大变化，商没有怎么增加；另一些企业扩张过程中商增剧烈，增到一定程度后`科斯定理`表明企业已无存在必要；从商增角度理解企业成长的成本项更本质，过去大量讨论企业靠什么吸收成长中的熵增。
-## 论点：投资框架反思之二——坚持终局判断的同时把握中期机会
-- **错过10倍机会**：肖楠因对某些企业终局判断悲观或看不清而放弃中期投资机会，包括10倍机会；复盘发现当时判断正确——产品领先确被竞争对手追上，但企业从当时到后来足足涨了十几倍，整个过程完全错过。
-- **反思结论**：在坚持终局重要性判断的基础上，也要争取研究格局演进的阶段性特征来把握投资机会；可通过紧密跟踪认知快速迭代、识别里程碑式事件来提高胜率，在中期时间内获得好的投资回报率。
-## 论点：投资框架反思之三——长期变量解释相当部分收益率来源
-- **国运变量**：肖楠提出“为什么日本、德国、越南没有出巴菲特、索罗斯，美国有”的问题；西方世界无人预料到中国和平稳定高速发展30多年、40年，这个隐藏的巨大变量可称作国运。
-- **茅台逻辑**：过去买茅台赚钱的人写的回忆录中，A说因为便宜、B说产品好、C说商业模式好，但这些逻辑加在一起无法解释过去十年、二十年茅台如此巨大的涨幅；可能有一个更大变量在起作用，如中国宏观经济背景、文化背景、品牌背景。
-- **制造业主导**：过去10年消费品领域（家电、快消可乐）慢慢被中国主导，制造业更不用说；中国在很多细分领域成为产业链主导，为什么偏偏是中国而非别的国家，这点非常有意思。
-- **保持谦卑**：穷尽所有智慧精力探究收益率来源，往往仍忽略巨大变量；很多基金经理说放在美国能挣更多钱，但放在日本、德国、新加坡能否挣这么多？未来研究会把十年维度上起作用的隐性长期变量纳入研究框架。
-- **奢侈品案例**：LV、爱马仕讲的故事是“祖上给皇上当过马夫、给娘娘当过皮匠”，但给的是英国、法国老牌资本主义国家的皇上娘娘，因其军舰当年横扫全世界；20年前天涯论坛问中国GDP何时超日本被群嘲，今天大家在算哪年超美国。
-- **白酒出海逻辑**：欧美人不喝白酒，普遍答案是“不好喝”，但30年前洋酒刚进中国时土豪兑雪碧喝，因难喝但为显示高档仍要喝——人家的文化是强势文化；若中国国力强盛到海军航母在人家十二海里外军事演习，就能讲“纯粮固态发酵才是好酒”的故事。
-## 论点：投资框架反思之四——深度价值可能长期无效
-- **深度价值只是结果**：肖楠认为深度价值只是一个结果，导致深度价值的原因不变，最好的结果也就是不输；去年投了一些认为是深度价值的标的，结果非常差，产生很大启发和刺激。
-- **打问号**：肖楠对“深度价值可能长期无效”打了问号，未得结论。
-## 论点：小企业X factor——驱动企业增长且不被线性描述的因子
-- **线性假设局限**：做DCF、DDM都是线性假设，无非增长率是12、13还是15、16、17的区别；但拉长到10年视角，企业发展是一条非常漂亮的曲线，经典投资模型没有一个变量隐含对企业发展曲率的估计。
-- **X factor定义**：大量行业、企业做着同样事情、生产差不多产品，差异巨大，原因是一些称作曲率的因素在起作用，肖楠将这些因素称作`X factor`；经典投资理论模型无法给这些因素定价，但长期起作用的就是这些。
-- **结论**：驱动企业增长且不被线性描述的因子，即使无法有效定价也一定要承认其存在；否则会陷入“企业挺好但估值贵、企业便宜但基本面烂”的挣扎。
-- **第二第三增长曲线**：5年前、10年前大家说某些企业产品渗透率已很高、利润率已很高，但到今天这些说法全部没实现，企业长出第二、第三增长曲线；超额认知就来自这些方面。
+- **知识与信息的区别**：肖楠认为，他看好某个板块或个股是基于相关知识（`knowledge`），而投资者得到的仅仅是一条“肖楠看好某某”的信息（`information`），两者之间存在巨大鸿沟。
+- **观点易变**：肖楠举例，他今天看好某板块，明天可能因新知识增加而修正判断，但投资者可能需要等一年甚至更长时间才知道观点已变。
+- **研究框架四象限**：肖楠将问题分为重要不重要、可研究以及难以研究四类，他真正关心的是标的基本面是否变化、投资逻辑是否更新、认知是否更深入领先、投资框架是否需修正，这些是可被研究的“富矿”。
+- **框架仅针对个人**：肖楠强调这张表仅针对他个人，例如基于宏观变量做资产配置的投资者，可能认为美联储利率变化对市场的影响是既重要又可研究的问题。
+## 论点：反对“抱团”说法，认为定义不本质
+- **定义不本质导致研究误入歧途**：肖楠以“光明使者”为例——若给一种动物起名“光明使者”，因太阳出来与动物叫没有因果关系，这个定义不本质，会导致误入歧途；同理，“抱团”只是现象，不说明问题。
+- **基金经理间是竞争关系**：肖楠指出，基金经理之间是竞争关系，主观上不可能商量好一起买某只股票，如打电话给嘉实基金王经理“抱在一起”买股票是不可能的，大家都想买跟别人不一样的东西并获市场认可。
+- **同一公司买同一板块不叫抱团**：肖楠认为，研究员推荐股票、多位基金经理认可后买入，是正常运作方式；若定义为抱团，难道要“抽取三位幸运基金经理”才能买？这显然荒谬。
+- **忽略时间维度**：肖楠指出，抱团是截面数据，忽略了时间维度；他举例8年前、5年前就买了某些股票，突然一大堆人蜂拥而至，但拉长时间看，A股和海外股市都有类似现象，如“五朵金花”“眉飞色舞”“长牛的医药消费”等，非常稀松平常。
+## 论点：反对“均值回归”，认为其是局部正确
+- **均值回归的定义与局限**：肖楠解释，均值回归就是“跌多了要涨，涨多了要跌”，短期看K线图确实如此，但拉长看无法解释10年涨10倍、20倍、50倍、100倍的长线牛股。
+- **商学院老师案例**：肖楠举例，某商学院老师在投资理论课上教学生，过去10年在海螺水泥上做波段赚了两三倍，2016或2017年卖出后等回调，结果两年涨了五六倍，再也没能买回来——**均值回归90%的时间正确，那10%的错误依然代价惨重**。
+- **收益率是幂律分布**：肖楠指出，收益率是幂律分布而非正态分布，做投资的核心是找到摆脱“涨多了要跌”规律的长线超级大牛股；**美国股市200年来的价值增量由4%的公司贡献**，若挖掉这4%的公司，200年来美国股市没有涨。
+## 论点：过去一年研究布局四大方向——互联网、财富管理、新消费、高端制造
+- **互联网**：全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业——第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多），未来仍会有大机会；开通港股通后，以前在A股无法投的公司现在可以投，不能容忍错失机会。
+- **财富管理**：中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，因巨大基数效应和收入分布密度效应，会有巨额剩余财富有待专业机构管理，行业潜在空间远超想象。
+- **新消费**：新一代消费公司从CEO的想法理念、组织架构、经营理念到生产方式、营销方式，完全不同于匮乏年代出来的传统企业；随着中国越来越富裕，这类公司会越来越多。
+- **高端制造**：中国是全球几乎唯一拥有全产业链的国家；在非常多的制造业细分领域，中国已不是被卡脖子，而是“占据主导地位”；与10年前“10亿双袜子换台飞机”的理解完全不同，欧美日企业可得的市场份额，从中国视角看“已经是中国企业碗里的肉”。
+## 论点：过去一年重要认知——新消费领域产品差异巨大，商增是理解商业模式的重要角度
+- **新消费产品差异**：肖楠举例，外人看两家公司产品差不多（卖笔、卖电饭锅），但收入利润体量差距巨大；深入研究发现，在产品经理和CEO眼中，自家产品与竞争对手产品存在巨大鸿沟，这些差异在三年、五年、十年维度会被放大。
+- **新消费行业格局**：传统消费行业龙头赚钱，龙二龙三也赚钱；新消费领域同样巨大的行业可能只有两家公司，一家赚很多钱，另一家完全不挣钱、不知怎么挣钱，差异极大。
+- **商增与商业模式**：肖楠提出从商增角度理解企业商业模式，企业成长过程中，有些企业商增速度远超另一些，商增过快导致企业走向失败；研究大量企业失败案例后，认为商增是理解商业模式的重要角度。
+## 论点：投资框架反思之一——世界上没有一劳永逸的坐地收钱生意
+- **三种商业模式分类**：肖楠过去将生意分为三类——坐地收钱（最喜欢买）、苦尽甘来、燃烧自己照亮别人（不值得买）；至今仍相信这一划分，但承认框架有不完备性。
+- **坐地收钱生意极稀缺**：肖楠指出，世界上没有一劳永逸的坐地收钱生意，哪怕爱马仕这样的企业，一个设计师的好坏也可能影响未来五年十年的销售；长期看所有企业都会死去，若单一从“买活得尽可能长的企业”维度出发，可能错失很多机会。
+## 论点：投资框架反思之二——从商增角度理解商业模式更本质
+- **商增与成长**：肖楠发现，有些企业从诞生到收入和利润涨100倍，结构跟诞生时没有特别大区别，商没有怎么增加就能放大100倍；另一些企业扩张过程中商增剧烈，商增到一定程度后，科斯定理告诉我们企业已没有存在必要。
+- **吸收熵增**：肖楠表示，过去一段时间大量讨论企业在成长过程中靠什么吸收熵增，从商增角度理解企业成长中的成本项，可能比传统商业模式分类更本质。
+## 论点：投资框架反思之三——存在长期变量影响收益率，需保持谦卑
+- **为什么美国出投资大师**：肖楠提出，为什么日本、德国、越南没有出巴菲特、索罗斯这样的投资大师，而美国有；中国股市发展20多年也诞生了长线收益非常好的基金经理，但放到台湾、日本、韩国未必有同样收益率——可能有特别长线的变量解释了相当一部分收益率来源。
+- **国运是隐藏的巨大变量**：肖楠指出，西方世界过去对中国判断中，没人预料到中国和平稳定高速发展30多年、40年，这是隐藏的巨大变量，称作“国运”有点对也有点不对。
+- **茅台案例**：肖楠举例，把过去买茅台赚钱的人写的回忆录中的逻辑（便宜、产品好、商业模式好）全部列出来，加在一起也解释不了过去十年、二十年茅台如此巨大的涨幅——可能有更大的变量（宏观经济背景、文化背景、品牌背景）在后面起作用。
+- **长期变量纳入研究**：肖楠表示，未来做研究时会把一些特别隐性的、可能在十年维度上起作用的长期变量纳入研究；如LV、爱马仕等奢侈品牌讲“祖上给皇上当过马夫、给娘娘当过皮匠”的故事，但给的是英国、法国老牌资本主义国家的皇上和娘娘，因为“他们家的军舰当年横扫全世界”——国力是品牌背后的长期变量。
+- **白酒出海逻辑**：肖楠认为，欧美人不爱喝白酒，答案“不好喝”可能不正确；30年前洋酒刚进入中国时，中国土豪兑雪碧喝，因为难喝但文化强势，为显示高档也要喝；若有一天中国国力强盛到海军航母在人家十二海里外做军事演习，就能讲“纯粮固态发酵的酒才是好酒”的故事。
+## 论点：投资框架反思之四——深度价值可能长期无效（打了问号）
+- **深度价值只是结果**：肖楠认为，深度价值只是结果，若导致深度价值的原因不变，最好的结果也就是“不输”；过去投了一些认为是深度价值的标的，包括去年投的，结果非常差，产生了很大启发和刺激。
+- **未得结论**：肖楠强调，深度价值是否长期无效，他打了问号，没有得出结论。
+## 论点：投资框架反思之五——提出X factor，驱动企业增长且不被线性描述的因子
+- **线性假设的局限**：肖楠指出，做DCF、DDM都是线性假设，无非增长率是12%、13%还是15%、16%、17%的区别；但拉长到10年视角，企业发展是一条曲线，经典投资模型中没有变量隐含对企业发展曲率的估计。
+- **X factor的定义**：肖楠将驱动企业增长且不被线性描述的因子称为`X factor`，经典投资理论模型无法给这些因素定价，但长期起作用的就是这些因素；即使无法有效定价，也一定要承认其存在，否则会陷入“企业挺好但估值贵、企业便宜但基本面烂”的困境。
+- **典型案例**：肖楠举例，5年前、10年前大家说某些企业产品渗透率已很高、利润率已很高，但到今天看当年说的都没实现，企业长出了第二、第三生长曲线——这些企业有X factor；**超额认知就来自于这些方面**。
+## 论点：对终局判断的反思——坚持终局重要性判断，同时争取把握中期投资机会
+- **错过十几倍涨幅**：肖楠反思，过去因判断某些企业终局不太好或看不清楚，放弃了中期投资机会，甚至错过10倍的投资机会；最打脸的是终局判断对了，却在两三年里错过十几倍涨幅。
+- **具体案例**：肖楠举例，某企业产品跨代领先竞争对手，当时判断领先不能长期保持、行业格局会变差、ROE会剧烈下降——这一判断在随后一两年被验证，但企业从下终局判断到后来足足涨了十几倍，整个过程完全错过。
+- **改进方向**：肖楠表示，未来可通过紧密跟踪认知快速迭代、识别里程碑式事件来改变投资逻辑，提高胜率，在中期时间内获得好的投资回报率；在坚持终局重要性判断基础上，争取研究格局演进的阶段性特征来把握投资机会。
+## 论点：对企业家精神的反思——谨慎归因，不轻易定价
+- **企业家定价困境**：肖楠提到与张坤争论企业家精神或企业家值不值得定价的问题；企业如日中天时说企业家优秀、估值给50倍，企业犯错时说企业家不行，导致无法给企业家定价。
+- **谨慎归因原则**：肖楠强调，评判企业家精神要特别小心谨慎，不要乱归因——不要因企业经营成功就说企业家特别厉害，就像不要因基金经理过去业绩好就说他特别厉害；要把能归因到数据里客观指标的因素全部归因完后，再谨慎评价虚的因素。
+- **不轻易定价**：肖楠表示，绝对不要说“因为企业家在，所以公司值多少”，要避免因对企业家认可而犯投资错误，底线风险一定要搞好；企业家精神等虚的因素，在所有客观归因尽量穷尽后再考虑。
+- **有限范围内比较**：肖楠指出，只能在有限范围内做两两比较——两家公司做同样生意、同样产品时，可比较企业家水平高低、理念先后，找认可的那一家；不要跨行业、跨业务、跨产品比较，不要什么事情都归结到企业家身上。
 # 金句总结
-&gt; “知识和信息之间是有着巨大的鸿沟的。”
-&gt; “务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。”
-&gt; “均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。”
-&gt; “收益率是幂律分布的，不是正态分布的。”
-&gt; “这个世界上其实没有一劳永逸的坐地收钱的生意。”
-&gt; “我们尽管穷尽了我们所有的智慧、所有的精力去力求探究我们的这个收益率的来源，往往依然是忽略了一个巨大的变量在后面起作用。”
-&gt; “驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。”
-&gt; “伟大公司是在财务指标里面看不出来的。”
+&gt; 知识和信息之间是有着巨大的鸿沟的。
+&gt; 背景：开场时肖楠总解释为何不直接回答投资者关心的“what happen next”问题——他拥有的是基于知识体系的判断，而投资者得到的只是一条信息。
+&gt; 务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。
+&gt; 背景：肖楠总在介绍以巴菲特为代表的“极端务实派”和以索罗斯为代表的“极端务虚派”两个投资流派时强调，理念本身没有好坏，关键在于执行。
+&gt; 均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。
+&gt; 背景：肖楠总在反对“均值回归”观点时，举例某商学院老师在海螺水泥上做波段十年赚两三倍，但2016/2017年卖出后两年涨五六倍、再未买回。
+&gt; 200年以来，美国股市的价值增量，是由4%的公司贡献的。
+&gt; 背景：肖楠总论证收益率是幂律分布而非正态分布时引用该数据，说明长线超级大牛股贡献了市场绝大部分收益率。
+&gt; 世界上其实没有一劳永逸的坐地收钱的生意。
+&gt; 背景：肖楠总反思其“坐地收钱、苦尽甘来、燃烧自己照亮别人”三种商业模式分类时承认，即使爱马仕也会受设计师好坏影响，单一维度可能错失机会。
+&gt; 我们尽管穷尽了我们所有的智慧、所有的精力去力求探究我们的收益率的来源，往往依然是忽略了一个巨大的变量在后面起作用。
+&gt; 背景：肖楠总在讨论“为什么日本没有出巴菲特、索罗斯”时指出，国运、文化背景等长期变量可能解释了相当一部分收益率来源，需对市场保持谦卑。
+&gt; 驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。
+&gt; 背景：肖楠总提出“X factor”概念时强调，经典投资模型无法为这些曲率因素定价，但它们在长期投资中至关重要。
+&gt; 伟大公司是在财务指标里面看不出来的。
+&gt; 背景：回答投资者关于伟大公司判断标准时，肖楠总举例A、B两家公司——A公司研发高、有产业报国情怀，堪称伟大，但这类特质无法从报表中读出。
 # Q&amp;A 环节
-**张楠**：有客户提问，您刚刚讲到在重视终局结果的过程中，也更加关注格局演进的阶段性特征和中期投资机会，能否再详细描述一下？
-**肖楠**：这个想法最早来自我们过去错过的一些特别大的机会，非常懊恼。我们之所以错过，是因为判断这些行业的终局可能不大行，但最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，当时完全可以在考虑终局可能没那么好的前提下，依然做出漂亮投资。这类企业有一个重要特征是我们当时忽略的：比如某一代产品当时领先，后来确实如我们所料被人追上，但企业深深做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。这让我们非常惊讶，刺激很大。所以后来我们在一些投资里，渐渐开始承认终局可能没那么强、没那么好，不会像一劳永逸躺着收钱那么强，但在这种终局判断下依然能做出好的投资，希望未来不要再错过类似机会。具体标的不太好在公开场合讲，确实有一两个标的给我们带来极大刺激。
+**张楠**：有客户提问，您刚刚讲到在重视终局结果的过程中，也更加关注格局演进阶段性的特征和中期投资机会，能否再详细描述一下？
+**肖楠**：这个想法最早来自我们过去错过了一些特别大的机会，非常懊恼。我们之所以错过，是因为判断这些行业的终局可能不大行，而最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，我们当时完全可以在考虑终局可能没那么好的前提下，依然做出漂亮投资。这类企业有个重要特征是我们当时忽略的：某一代产品当时领先，后来确如我们所料被人追上，但企业深深做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。所以我们在后来的投资里，渐渐开始接受终局可能没那么强、不会像一劳永逸躺着收钱那么强，但依然能做出好的投资。具体标的不太好在公开场合讲，确实有一两个标的给我们带来极大的刺激。
 **张楠**：您在年报中也讲到过坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有一些具体的财务指标？
-**肖楠**：伟大公司在财务指标里面是看不出来的。个股没办法在公开场合具体说，我举一个例子：有两家公司都很厉害，同属一个大行业但不同细分子行业，投资逻辑非常像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高。但有一点不一样——B公司不怎么研发，产品能做到成本极低，靠的是管理上精益求精，业内络绎不绝来学习但不太学得会，非常有壁垒；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人、日本人手里。有意思的是这两家都是国企，A公司在发展初期被德国人、日本人狠狠坑过，从董事长到总经理到技术骨干都积攒了非常强烈的产业报国、技术报国的理想，从跟着日本人学、德国人学，到越做越强超越对手，到对手跑过来跟他们学，到开始做全产业链布局——把这些写下来就是一个产业史诗般壮丽的东西，这种企业堪称伟大。过去在这个领域很多是日本人、美国人、台湾省的企业家占据，你会看到中国人在一点点往前拱，这些人不是想今年赚3个亿5个亿，而是一门心思往前做。如果有机会，未来可能把这些企业的经历写出来。
+**肖楠**：伟大公司是在财务指标里面看不出来的。我举一个例子，不能说具体哪个企业：A企业和B企业同属一个大行业但不同细分子行业，投资逻辑非常像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高。区别在于，B公司没有太多研发，靠管理上精益求精做到成本极低，壁垒是业内络绎不绝来学习但学不会的管理能力；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人、日本人手里。有意思的是这两家都是国企，A公司在发展初期被德国人、日本人狠狠坑过，从董事长到技术骨干积攒了非常强烈的产业报国、技术报国的理想，从跟着学、越做越强、超越对手，到对手跑过来跟他们学，再到做全产业链布局，写下来就是产业上史诗般壮丽的东西，这种企业堪称伟大。过去能看到非常多这样的企业，以前领域里是日本人、美国人、台湾省企业家占据，中国人在一点点往前拱，这些人不是想今年赚三五个亿，而是一门心思往前做。
 **张楠**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对于消费以外的行业选股，主要基于什么逻辑？
-**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的"不可能三角"、企业三阶段、三种商业模式那一类。只不过消费行业基金只许买消费，不能买别的，所以肯定在消费行业里面选。两个的选股逻辑完全一样，没有什么区别。
-**张楠**：您怎么看待血制品行业的竞争壁垒？
-**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开了，因为我们的研究不是特别深入。我们也找了一堆强壁垒的公司，相比之下买了另外一些。
-**张楠**：在管理行业能否再具体讲一下？
+**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的不可能三角、企业的三阶段、三种商业模式。只不过消费行业只许买消费，不能买别的，所以肯定在消费行业里面选。两个的选股逻辑完全一样，没有什么区别。
+**张楠**：您是怎么看待血制品行业的竞争壁垒呢？
+**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开了，因为我们的研究不是特别深入。我们也找了一堆强壁垒的公司，相比之下买了另外的一些。
+**张楠**：在管理行业能否再具体讲一下呢？
 **肖楠**：我们只就血制品这个行业，研究得不是特别多。因为我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有一些特别冲突的观点。
-**张楠**：农林牧渔行业有所提升，请问您对这个行业的观点？
-**肖楠**：这行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。我们不能在公开场合讲具体股票的投资逻辑。不是我先看好农林牧渔行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。
-**张楠**：您能否再具体讲一下生意模式里边商增和商减的分析？
-**肖楠**：用直白的理论讲，你们都在不同机构、企业里面，都是打工人，可以深切感受到：企业从小到大，部门越来越多，以前三五个部门现在十几个，中层干部一大堆，上面分领导、副总裁，下面一大堆基层部门，传达效率变低，内部腐败开始出现。企业为了解决这些问题，要设置部门去巡视检查，又多了一个部门；部门里的人干了三五年要加工资、提级别，这么多部门老总今年提哪个、明年提哪个。企业发展到一定程度要多做业务，往下游做或往上游做，多一项业务就要多一个副总裁，又有很多部门。你会发现有些生意模式收入10个亿跟100个亿时没多多少机构、没多几个部门，有些企业不需要设置那么多副总裁和高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如有些行业就剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生——后者从一开始就没考虑好企业大了以后商增怎么处理。而另一家基本是高度中央集权，CEO有一个非常强大的情报部门，知道公司每一件重要事情细入到基层是怎么回事。我特别建议大家去读一读党史，看看这个国家怎么从国民革命时期、抗战时期一直走到现在，组织到今天还能保持活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年，这种事情在很多国家都会发生。
-**张楠**：您讲到伟大企业的增长曲线，能否对曲线的情况再具体讲一下？
-**肖楠**：比如你过去几年每年看，这个企业今年增长20%、明年15%、后年17.5%，都是线性的，有些年份差一点增长3%、5%。突然有一天你站10年周期看，这个企业跟竞争对手之间拉开了极大差距。举个例子，快递行业，疫情的时候只有顺丰能送，没有疫情你看不出来，一下子顺丰的估值和业绩把竞争对手甩出一大截。如果做线性外推，无非你说今年增速快一点，你15%、别人13%，但拉长看就是在一些关键点上突然甩出来。家电领域也是，过去格力一直是老大，美的一直在做渠道扁平化、T+3，一直没看到成果，突然疫情来了，美的的占有率哗一下就上去了，一下子超过格力。当一些企业在埋头做事情、还没体现到报表的时候，我们往往就忽略这些事情未来可能产生的特别重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的，平时一年一年看是直线发展，今年增长3%、明年5%，就在有一些点子上人家一下子出来——平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞，这样的企业就特别厉害。
+**张楠**：农林牧渔行业持仓有所提升，请问您对这个行业的观点能讲一下吗？
+**肖楠**：这行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。不是我先看好农林牧渔行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。具体股票的投资逻辑不能在公开场合讲。
+**张楠**：您能够再具体讲一下生意模式里边商增和商减的分析吗？
+**肖楠**：用直白的话讲，你们自己在企业里都是打工人，可以深切感受到：企业从小到大，部门越来越多，以前三五个部门现在十几个，中层干部一大堆，上面分领导、副总裁，下面一大堆基层部门，传达效率变低，内部腐败开始出现。企业为了解决腐败问题，要设巡视检查部门，又多一个部门；部门里的人干三五年要加工资提级别，这么多部门老总今年提哪个、明年提哪个。企业发展到一定程度要扩张，往下游做或往上游做，多一项业务就多一个副总裁、多很多部门。有些生意收入10个亿跟100个亿时没多几个部门，有些企业不需要设那么多高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如有些行业剩两家互联网大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生——后者从一开始就没考虑好企业大了以后商增怎么处理。而另一家基本是高度中央集权，有非常强大的情报部门，CEO知道每一件重要事情细入到基层是怎么回事。我特别建议大家去读一读党史，看看这个组织怎么从国民革命时期、抗战时期一直走到现在，到今天还能保证这样的活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年这种事在很多国家都会发生。
+**张楠**：您讲到伟大企业的增长曲线，能否再具体跟大家讲一下？
+**肖楠**：有些企业你每年看都是线性的，今年增长20、明年15、后年17.5，差的时候增长3、增长5。突然有一天你站10年周期看，这个企业跟竞争对手之间拉开了极大差距。举个例子，快递行业，疫情的时候只有顺丰能送，没疫情时你看不出来，一下子顺丰的估值和业绩把竞争对手甩出一大截。家电领域也是，过去格力一直是老大，美的在做渠道扁平化、T+3，一直没看到成果，突然疫情来了，美的占有率哗一下就上去了，一下子超过格力。当一些企业在埋头做事、还没体现到报表的时候，我们往往忽略这些事未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的——平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞。
 **张楠**：由于时间关系，最后两个问题。您刚刚讲到财富管理行业，能否对这个行业具体展开，讲一下投资逻辑和投资机会？
-**肖楠**：财富管理行业这个话题特别大，而且行业是分层的，顶级富豪的财富管理怎么管、普通中产阶级怎么做、中低收入人员怎么做，都有不同的公司和商业模式，说起来超级复杂。我们最早关注这个行业，其实是研究保险时发现一些有意思的事情：某些保险公司一个保险员一单能签七八千的首年保费，有些保险公司平均一个业务员大概三千多、有些两千多，差距巨大。我们花了很多时间调研特别厉害的销售和中等销售人员，发现同样是卖保险，背后的逻辑和机制差异超级大，而这些公司的结构设置、激励机制、文化又有巨大差异。去年基金非常火，我们发基金时发现，有些渠道经理过来调研问的问题超级专业，另外一些渠道经理问的问题永远是下半年是涨是跌、明年是牛市还是熊市。同样在这个行业混的人，最后拿出的经营结果差距巨大，后面的模式又超级不一样。财富管理行业最大的逻辑在于财富分布超级不均匀，所以有些头部公司真的一口气拿掉这个行业增量的绝大部分，而有些公司只能拿到剩下的20%的80%。在这种特别偏激、特别幂律分布的行业里，就有可能诞生出特别大的企业。很遗憾，我们有一些产品因为监管和法律规则的原因反而不能投类似标的，但未来合同设置更清晰的时候，我们可能会在这方面的投资上有所体现。
-**张楠**：您刚刚讲到曲线方面，第二第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
-**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营成功就说这个企业家特别厉害，就像不要因为一个基金经理过去业绩很好就说他特别厉害一样。一定要把所有能够归因到数据里、客观指标里的因素全部归因完，再特别谨慎地评价一些比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为这个企业家在，所以这个公司就能值多少多少。我始终强调的是避免错误的归因，避免因为你对企业家的认可去犯投资上的错误，一定要把底线的风险搞好。我们一致同意这个东西不可被定价。这些代表曲率的因素、X factor、技术进步、企业家精神，什么时候考虑它？是在所有客观归因都尽量穷尽以后，我们说可能某种程度上一些收益率的归因可能归到这里面去。第二点，确确实实你只能在有限范围内做两两比较——比如两家公司做同样一个生意、同样产品，在这种限定条件下比较两个企业家的水平高低、理念先后，找你认可的那一家，仅此而已，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，一定要谨慎地使用所谓企业家精神、伟大企业这些词，在一些特别极端的时候，它可能是你某些信仰上的支持，但尽量不要去用。</t>
+**肖楠**：财富管理行业这个话题特别大，而且行业是分层的，顶级富豪的财富管理、普通中产阶级、中低收入人员的财富管理，都有不同的公司和商业模式。我们最早关注这个行业是研究保险时发现的：有些保险公司一个保险员一单能签七八千的首期保费，有些公司平均一个业务员只有两三千，差距巨大。我们调研了特别厉害的销售和中等销售，发现同样是卖保险，背后的逻辑、机制差异超级大，而这些差异来自公司的结构设置、激励机制、文化等。去年基金很火，我们发基金时同样发现：有些渠道经理过来调研，问的问题超级专业；另外一些渠道经理问的永远是下半年是涨是跌、明年是牛市还是熊市。同样在这个行业混的人，经营结果差距巨大。财富管理行业最大的逻辑在于财富分布超级不均匀，头部公司可能一口气拿掉行业增量的绝大部分，比如第一名拿掉增量的70%、80%，第二名只能拿到剩下20%的80%。在这种特别偏激、幂律分布的行业里，有可能诞生出特别大的企业。很遗憾我们有一些产品因为监管和法律规则的原因反而不能投类似的标的，未来合同设置更清晰时，可能会在这方面的投资上有所体现。
+**张楠**：您讲到第二、第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
+**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营的挺成功就说这个企业家特别厉害，就像不要因为一个基金经理过去业绩很好就说他特别厉害一样。一定要把所有能够归因到数据里客观指标的因素全部归因完，再特别谨慎地去评价一些比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为这个企业家在，所以这个公司就能值多少多少。我始终强调的是避免错误的归因，避免因为对某个企业家的认可去犯投资上的错误，一定要把底线的风险搞好。我们一致同意的就是这些东西不可被定价。像曲率因素、X factor、技术进步、企业家精神这些比较虚的因素，什么时候考虑？是在所有客观归因都尽量穷尽以后，才说可能某种程度上一些收益率的归因归到这里面去。另外，只能在有限范围内做两两比较：两个公司做同样生意、同样产品，在这种限定条件下比较两个企业家水平的高低、理念的先后，去找你认可的那一家，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，要谨慎地使用所谓企业家精神、伟大企业这些词，在一些特别极端的时候，它可能是某些信仰上的支持，但尽量不要去用。</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>88.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26252/8794</t>
+          <t>26252/9058</t>
         </is>
       </c>
     </row>
@@ -9193,51 +9087,46 @@
       <c r="C26" t="inlineStr">
         <is>
           <t># 辩论内容概述
-本次辩论赛围绕“拥有让人爱上自己的超能力是否美好”这一辩题展开，正方为RUC棒辩论队，反方为对方辩友。正方主张超能力客观存在，类比月老、丘比特，认为超能力能成就真爱，且掌握在爱你的人手中比掌握在蒙眼小孩手中更好；反方则反驳称超能力剥夺对方自由意志，本质是占有而非爱，并类比强奸、洗脑。双方就爱的本质、自由意志、洗脑与占有、放手的爱等核心议题展开交锋，正方在质询与小结环节逐步占据优势，最终获胜，获得4分钟小结时间。
+本次辩论赛围绕“拥有让人爱上自己的超能力是否美好”展开，正方为RUC棒辩论队，反方为对方辩友。正方主张超能力类比月老、丘比特，能让有情人终成眷属，成就真爱；反方则认为超能力剥夺对方自由意志，本质是占有而非爱，类比强奸、洗脑。辩论整体走向围绕“爱是否自由意志的产物”“超能力机制是否为洗脑”“珍惜程度取决于什么”等核心议题交锋，正方在质询与自由辩论中逐步占据主动，最终正方获胜，获得4分钟小结时间。
 # 核心论点
-辩题为“拥有让人爱上自己的超能力是否美好”，正方主张超能力能成就真爱，反方认为其剥夺自由意志、本质是占有。双方立论框架、核心论点与支撑论据详见下表。
+辩题为“拥有让人爱上自己的超能力是否美好”，正方主张超能力可成就真爱，反方认为其剥夺自由意志、本质是占有。双方立论框架、核心论点与支撑论据详见下表。
 | 阵营 | 立论框架 | 核心论点 | 支撑论据 |
 | --- | --- | --- | --- |
-| 正方 | 超能力客观存在，类比月老、丘比特，能成就真爱 | 超能力能成就真爱 | 月老和丘比特让有情人终成眷属；超能力掌握在爱你的人手中比掌握在蒙眼小孩手中更好 |
-| 正方 | 爱非自由意志产物 | 爱是身不由己的 | 用“坠入爱河”而非“跳入爱河”论证；爱一个人就是自己意志的产物 |
-| 正方 | 珍惜程度取决于认真对待 | 珍惜程度与新鲜感无关 | 恋爱过程当中真不珍惜对方取决于你到底有多认真的对待这种感情 |
-| 反方 | 超能力剥夺自由意志 | 超能力本质是占有而非爱 | 类比强奸、洗脑；强迫对方爱自己是违背意志 |
-| 反方 | 超能力机制是洗脑 | 洗脑不是爱，且无法获得真爱 | 洗脑错误，真的能够换回真爱；要么不爱他，要么你用了他也不可能真正获得对你的爱 |
+| 正方 | 超能力类比月老、丘比特，成就真爱 | 爱不是自由意志的产物 | 用“坠入爱河”而非“跳入爱河”佐证；超能力机制可能不是洗脑，而是改变自己或创造100%符合对方需求的人；珍惜程度取决于认真对待感情，而非获得爱的难易；若相处不合适会放手，但不用超能力会留下遗憾 |
+| 反方 | 超能力剥夺自由意志，本质是占有 | 超能力剥夺对方自由意志，类比强奸、洗脑 | 洗脑能否换来真爱，可能只是服从；强调保留被爱者的选择空间；质疑爱来得太容易会变质 |
 # 环节交锋
 ## 开篇立论
-- 正方提出超能力客观存在，类比月老、丘比特，认为超能力能成就真爱，且掌握在爱你的人手中比掌握在蒙眼小孩手中更好。
-  &gt; “月老和丘比特他让有情人终成眷属。”
-- 反方反驳称超能力剥夺对方自由意志，本质是占有而非爱，并类比强奸、洗脑。
-  &gt; “这个超能力抹杀了对方的这个决定。”
+- 正方将超能力类比月老、丘比特，认为其让有情人终成眷属，成就真爱；反方反驳称超能力剥夺对方自由意志，类比强奸、洗脑，本质是占有。
+  &gt; “这个超能力抹杀了对方的这个决定，这是第一点。”
+- 正方提出爱不是自由意志的产物，用“坠入爱河”而非“跳入爱河”佐证；反方质疑洗脑能否换来真爱，可能只是服从。
+  &gt; “什么叫做情非得已，什么叫做情感意境，为什么我们在描述恋爱的感觉的时候，我们说的是坠入爱河，而不是说去跳入爱河。”
 ## 质询环节
-- 正方质询反方：超能力是否剥夺自由意志，反方回应称超能力是操控自由意志，类似洗脑。
-  &gt; “你觉得我们这个超能力就是操控他的自由意志，有点像给他洗脑。”
-- 反方质询正方：超能力是否违背对方意志，正方回应称爱非自由意志产物，用“坠入爱河”而非“跳入爱河”论证。
-  &gt; “为什么我们在描述恋爱的感觉的时候，我们说的是坠入爱河，而不是说去跳入爱河。”
-- 正方质询反方：超能力机制未必是洗脑，反方回应称洗脑不是爱，且洗脑无法获得真爱。
-  &gt; “洗脑真的是爱吗？第二期呢我真的能获得爱吗？”
+- 正方质询反方：超能力机制可能不是洗脑，而是改变自己或创造100%符合对方需求的人；反方回应称洗脑就是爱吗，质疑其本质。
+  &gt; “可不可以是我打了强纸之后，生了一张他100%会爱上我的脸。”
+- 反方质询正方：超能力剥夺对方选择权，类比强奸违背妇女意志；正方回应称爱跟自由意志无关，需证明其相关。
+  &gt; “强奸这件事情叫做违背妇女意志，强行发生性关系，而今天在面对情况当中，为什么是违背对方意志，强行介入亲密关系。”
 ## 自由辩论
-- 反方提出“放手的爱”，正方回应称若相处后不合适会放手。
-  &gt; “如果这个时候真的是相处之后，我也觉得我跟他没有办法在一起，那这个时候爱的信号就是我会再用这个超能力。”
-- 正方质疑反方“珍惜程度取决于新鲜感”的观点，反方回应称珍惜取决于认真对待。
-  &gt; “我们最能够让爱保鲜的方式就是在恋爱过程当中相互忽略。”
+- 正方提出珍惜程度取决于认真对待感情，而非获得爱的难易；反方质疑若爱来得太容易会变质。
+  &gt; “难道我们在恋爱过程当中珍不珍惜对方这件事情完全看我们之间的新鲜感？”
+- 反方提出“放手的爱”概念，正方回应称若相处不合适会放手，但不用超能力会留下遗憾。
+  &gt; “如果我一开始没有用这个超能力，那我今后再面对任何一段感情的时候，我都会想，如果我当初用了这个超能力，是不是我身边的人就会是我自己那个人？”
+- 反方强调保留被爱者的选择空间，正方认为掌握在爱你的人手里比蒙眼小孩好。
+  &gt; “我方认为掌握在一个爱你的人手里，比掌握在一个蒙眼的小孩子手里来的好的。”
 ## 小节总结
-- 正方总结称超能力掌握在爱你的人手中，比掌握在蒙眼小孩手中更好。
-  &gt; “我方认为掌握在一个爱你的人手里，比掌握在一个蒙眼的小孩子手里来的好的。”
-- 反方总结称超能力剥夺对方自由意志，本质是占有而非爱。
-  &gt; “你通过占有的方式获得他的爱呀，这才是你的超能力嘛。”
+- 正方总结指出反方未论证爱是自由意志的产物，且超能力机制未必是洗脑；反方则质疑洗脑能否换来真爱。
+  &gt; “到目前为止，对方都没有向我们论证，在您方的世界里，我只要意志在爱这个人，到底发生怎样的作用。”
 # 结辩与评委点评
-- **正方结辩**：正方强调超能力掌握在爱你的人手中，比掌握在蒙眼小孩手中更好，且爱非自由意志产物，珍惜程度取决于认真对待而非新鲜感。正方最终获胜，获得4分钟小结时间。
-- **反方结辩**：反方强调超能力剥夺对方自由意志，本质是占有而非爱，类比强奸、洗脑，认为强迫对方爱自己是违背意志。
-- **评委点评**：评委未给出具体点评，但正方最终获胜，获得4分钟小结时间。</t>
+- **正方结辩**：正方总结指出反方未论证爱是自由意志的产物，超能力机制未必是洗脑，更可能是改变自己或创造100%符合对方需求的人；珍惜程度取决于认真对待感情，而非获得爱的难易。正方获胜，获得4分钟小结时间。
+- **反方结辩**：反方强调超能力剥夺对方自由意志，本质是占有而非爱，类比强奸、洗脑；质疑洗脑能否换来真爱，可能只是服从；强调保留被爱者的选择空间。
+- **评委点评**：评委未作明确点评，仅宣布正方获胜，获得4分钟小结时间。</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>35.3</v>
+        <v>36.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12403/1624</t>
+          <t>12403/1659</t>
         </is>
       </c>
     </row>
@@ -9594,35 +9483,36 @@
       <c r="C27" t="inlineStr">
         <is>
           <t># 就诊概况
-患者为女性，年龄、职业未提及，系结肠癌术后转移患者。本次就诊为家属（发言人1）携患者咨询医生（发言人2），围绕患者结肠癌术后化疗后出现肝、肺、腹膜转移的后续治疗方案展开讨论。核心主诉为患者2023年9月因腹痛确诊结肠癌并接受切除手术，术后完成8期化疗，复查发现肝转移，去年9月行肝消融及乳腺结节切除，3月底复查发现肝、肺、腹膜转移。初步判断为结肠癌术后多发转移，当前治疗以全身系统治疗为主，建议二次基因检测以精准选择靶向和免疫治疗。
+患者为结肠癌术后转移患者，于2023年9月因腹痛确诊结肠癌，行结肠癌切除术后接受8期化疗。本次就诊为家属与医生讨论后续治疗方案，核心主诉为复查发现肝、肺、腹膜转移，家属询问除化疗和靶向治疗外是否有更有效手段。初步判断需优先进行全身系统治疗，并建议二次基因检测以指导靶向和免疫治疗。
 # 病史与背景
-- **现病史**：患者2023年9月因肚子疼突然发作，疼了一晚上，确诊结肠癌后行结肠癌切除手术，术后完成8期化疗。
-- **转移与治疗经过**：复查发现肝转移，从老家来北京做PET-CT；去年9月行肝消融和乳腺结节切除，切肠时可能有腹膜转移，切得可能不干净；消融和乳腺结节切除后做了紫荆化疗，但只有第一次检查，后面因肝功能不行停用部分化疗药，中间停药3个月；3月底复查发现肝、肺、腹膜转移。
-- **既往史**：患者肠胃较弱，吃海鲜易上吐下泻，一直被认为肠胃比较弱。
-- **近期用药**：化疗药（具体药名未提及），因肝功能不佳停用其中一种；靶向药（具体药名未提及），3月底复查后情况未明确。
+- **现病史**：2023年9月因肚子疼确诊结肠癌，行结肠癌切除术后接受8期化疗；复查发现肝转移，去年9月行肝消融及乳腺结节切除；术后因肝功能不佳停用部分化疗药，中间停药3个月；3月底复查发现肝、肺、腹膜转移，4月份检查显示广泛性转移。
+- **既往史**：患者多年来肠胃较弱，吃海鲜易上吐下泻。
+- **手术史**：结肠癌切除手术、肝消融、乳腺结节切除。
+- **近期用药**：紫荆化疗（仅第一次检查，后因肝功能不行停用）；靶向治疗（3月底前使用）。
 # 诊断与检查结果
-- **诊断结论**：结肠癌术后多发转移，累及肝、肺、腹膜，肠壁可能受累。
-- **关键检查**：PET-CT显示肝转移、肺转移、腹膜转移；上个月（4月）肠镜显示没事，但PET显示有，医生认为可能是肠镜做得不好；医生提到肝上有小红帽（可能指病灶），美妆也有小红帽（可能指转移灶）。
-- **基因检测**：医生建议做二次基因检测，第一次基因检测可能不常见，第二次检测可能提供更多信息；检测可通过血液、尿液、唾液等完成，肿瘤医院检测可能更专业；医生提到基因检测的敏感性可能比正常人高3倍5倍。
-- **免疫评估**：医生提到可做免疫评估，但方案由家属决定；患者今天早上查了血。
+- **诊断结论**：结肠癌术后转移，目前肝、肺、腹膜均有转移，属于广泛性转移。
+- **关键检查**：PET-CT显示肝、肺、腹膜转移；上个月肠镜显示没事，但PET显示有转移，可能肠镜做得不好。
+- **异常指标**：肝功能不佳，导致化疗药物停用。
 # 治疗方案与医嘱
-- **检查安排**：建议做二次基因检测，以确认基因突变情况，指导精准选药；可在肿瘤医院做，可能更专业；医生提到如果外科手术发现有基因突变，基本上可以确定。
-- **治疗原则**：当前主要问题是全身系统治疗，包括化疗、靶向、免疫治疗；靶向和免疫联合可能协同增效（1+1），可尝试；如果肿瘤涨幅10公分，可能需要介入治疗，但目前不是主要问题。
-- **生活方式**：建议提升免疫力，靠自己调整状态；医生提到四联康（可能指益生菌），但患者没关注。
-- **复诊与陪同**：医生建议让患者把状态调整好，再做免疫评估，方案由家属决定；家属询问是否需要再做核磁，但不想做太多检查，医生未强制要求，偏向尊重患者意愿。
+- **检查安排**：建议进行二次基因检测，可在肿瘤医院做，大概有3个学科；医生提到基因检测可通过血液、尿液、唾液等样本进行。
+- **用药**：系统治疗包括化疗、靶向、免疫，可相加；靶向和免疫治疗可能协同，1+1&gt;2；医生提到免疫加靶向药（菲尼）的联合方案。
+- **生活方式**：建议提升免疫力，主要依靠患者自身；医生提到四联康（益生菌）可用于肠道不适。
+- **复诊与陪同**：建议进行免疫评估，但尊重患者意愿，方案由家属定。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
+| 紫杉醇（紫荆化疗） | 未提及 | 未提及 | 化疗 | 肝功能不佳时停用 |
+| 靶向药 | 未提及 | 未提及 | 口服或静脉 | 肝功能不佳时停用 |
+| 菲尼（结肠三线药） | 未提及 | 未提及 | 未提及 | 与免疫联合可能协同 |
 # 复诊与预警信号
-- **复诊时间**：未提及具体复诊时间。
-- **预警症状**：⚠️ 患者肝功能不佳，导致部分化疗药停用，可能影响治疗效果；⚠️ 患者有腹膜转移，切肠时可能切得不干净，存在复发风险；⚠️ 基因检测可能不够快，影响治疗决策。</t>
+未提及</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>40.6</v>
+        <v>37.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7063/1330</t>
+          <t>7063/953</t>
         </is>
       </c>
     </row>
@@ -9785,40 +9675,39 @@
       <c r="C28" t="inlineStr">
         <is>
           <t># 产品概况
-海尔洗衣机创新发布会于海尔洗衣机用户研发中心举行，发布洗干集成新物种叠黛H2。叠黛H2是海尔为中国家庭打造的原创之作，专为客阳一体空间设计，一体集成机身，解决洗烘套叠放带来的震动等安全隐患，高度降为167厘米，超薄机身可完美嵌入60厘米标准橱柜，全平不突出。产品以屏幕为核心，可操控洗涤、烘干和护理等多种模式，搭载全新升级的智慧大脑与中枢神经式智能网络，独有灵犀洗烘联动实现数据共享，洗涤结束前上桶提前15分钟主动预热以缩短烘干时长。叠黛H2搭载原创双擎热泵技术、行业领先的3D透视烘干、升级精华洗2.0（39分钟洗净一周衣物）、空净过滤系统及三台变频电机，实现低噪音、无残留、无毛絮。产品以诚意定价发布：10kg 3D透视烘干款12998元，10kg 净净双擎热泵款10998元。
+海尔洗衣机创新发布会于海尔洗衣机用户研发中心举行，发布洗干集成新物种叠黛H2。叠黛H2是海尔为中国家庭打造的原创之作，专为客阳一体空间设计，以一体集成机身解决洗烘套装叠放带来的震动等安全隐患，高度降至167厘米，超薄机身可嵌入60厘米标准橱柜，全平不突出。产品以屏幕为核心，可操控洗涤、烘干和护理等多种模式，搭载灵犀洗烘联动、原创双擎热泵技术、3D透视烘干、精华洗2.0、空净过滤系统与三台变频电机，实现洗烘联动、高效洗净、除毛絮、低噪音等体验升级。叠黛H2的目标人群是向往整洁有序新阳台的中国家庭，尤其是年轻人与养宠、有宝宝的家庭，旨在让用户告别晾晒、享受家的整洁有序。
 # 市场定位与目标用户
-叠黛H2面向向往整洁有序新阳台的中国家庭，尤其适合年轻人、养宠家庭和有宝宝的家庭。典型使用场景为客阳一体空间，用户在此休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间。原文指出，在欧洲滚筒洗衣机发源地，许多家庭有独立洗衣房，洗烘套装并排摆放；而在中国，80%的用户把洗烘套装放在阳台叠放使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便。叠黛H2针对这一差异，以一体集成机身、167厘米高度、60厘米标准橱柜嵌入、同向开门与无水盒设计，解决叠放痛点。原文未提及同类产品或上代产品对比。
+叠黛H2的目标人群是向往整洁有序新阳台的中国家庭，尤其是年轻人、养宠家庭和有宝宝的家庭。典型使用场景为客阳一体风格的阳台，年轻人在这里休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间，叠黛H2帮助用户彻底告别晾晒。原文指出，在欧洲滚筒洗衣机发源地，许多家庭有独立洗衣房，洗烘套装并排摆放；而在中国，80%的用户把洗烘套装放在阳台叠放使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便。叠黛H2针对中国阳台叠放痛点，以一体集成设计解决安全隐患并提升美观整洁，与洗烘套装的貌合神离不同，H2独有的灵犀洗烘联动实现数据共享，让烘干和洗涤无缝连接。
 # 核心卖点与技术参数
-## 空间集成
-- **一体集成机身**：专为客阳一体空间设计，解决洗烘套叠放带来的震动等安全隐患，高度降为**167厘米**，不用踮脚即可操作。
-- **超薄嵌入**：机身完美嵌入**60厘米标准橱柜**，全平不突出，让阳台更美观整洁。
+## 一体集成设计
+- **一体集成机身**：专为客阳一体空间设计，解决洗烘套叠放带来的震动等安全隐患，高度降为**167厘米**，不用踮脚操作。
+- **超薄机身**：完美嵌入**60厘米**标准橱柜，全平不突出，让阳台更加美观整洁。
 - **同向开门**：尊重使用习惯，取放衣物流畅自如；采用**无水盒设计**，无需手动倒水。
-## 智能联动
-- **智慧大脑**：以屏幕为核心，可全面操控洗涤、烘干和护理等多种模式，利用中枢神经式智能网络让上下桶默契配合。
-- **灵犀洗烘联动**：H2独有，实现数据共享，烘干和洗涤无缝连接；洗涤结束前上桶提前**15分钟**主动预热，缩短烘干时长。
+## 智慧互联
+- **智慧大脑**：H2全新升级，利用中枢神经式智能网络，让上下桶默契配合。
+- **灵犀洗烘联动**：H2独有，实现数据共享，烘干和洗涤无缝连接；洗涤结束前，上桶提前**15分钟**主动预热，缩短烘干时长。
 ## 烘干技术
 - **原创双擎热泵技术**：大件烘干不缠绕。
-- **3D透视烘干**：行业领先黑科技，羽绒服、水洗被均可一次烘透，免去二次晾晒。
-## 洗涤与健康
-- **精华洗2.0**：激活洗衣液，**39分钟**洗净一周衣物；新鲜净水漂洗减少洗衣液残留，对残留泡沫敏感人群友好。
-- **空净过滤系统**：去除衣物线屑和毛絮，洗衣无残留、干衣无毛絮，适合养宠家庭和有宝宝的家庭。
-- **三台变频电机**：洗涤、甩干、烘干全过程噪音低，享受安静陪伴时光。
+- **3D透视烘干**：行业领先黑科技，羽绒服或水洗被可一次烘透，免去二次晾晒。
+## 洗涤技术
+- **精华洗2.0**：激活洗衣液，**39分钟**洗净一周衣物。
+- **新鲜净水漂洗**：减少洗衣液残留，对残留泡沫敏感者是福音。
+## 健康与静音
+- **空净过滤系统**：去除衣物线屑和毛絮，适合养宠家庭；洗衣无残留，干衣无毛絮，适合有宝宝的家庭。
+- **三台变频电机**：洗涤、甩干、烘干全过程噪音低。
 | 维度 | 本产品 | 上代/竞品 | 提升 |
 | --- | --- | --- | --- |
-| 空间集成 | 一体集成机身，高度167厘米，嵌入60厘米标准橱柜，全平不突出，同向开门，无水盒设计 | 未提及 | 解决洗烘套叠放震动隐患，操作更便捷，阳台更美观整洁 |
-| 智能联动 | 智慧大脑+中枢神经式智能网络，灵犀洗烘联动，上桶提前15分钟预热 | 未提及 | 烘干洗涤无缝连接，缩短烘干时长 |
-| 烘干技术 | 原创双擎热泵技术，3D透视烘干 | 未提及 | 大件烘干不缠绕，羽绒服、水洗被一次烘透，免二次晾晒 |
-| 洗涤与健康 | 精华洗2.0，39分钟洗净一周衣物；空净过滤系统；三台变频电机 | 未提及 | 减少洗衣液残留，去除线屑毛絮，低噪音 |
+| 一体集成设计 | 一体集成机身，高度167厘米，超薄嵌入60厘米橱柜，全平不突出 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决震动安全隐患，操作更便捷，阳台更美观整洁 |
 # 定价与发售信息
-叠黛H2定价：10kg 3D透视烘干款**12998元**，10kg 净净双擎热泵款**10998元**。原文称这是对平嵌超薄产品「诚意满满的定价」。发售时间、购买渠道与预售政策未提及。</t>
+叠黛H2两款配置定价：**10kg 3D透视烘干款12998元**，**10kg 净净双擎热泵款10998元**。发言人表示，为这款平嵌超薄产品拿出了诚意满满的定价。发售时间、购买渠道与预售政策未提及。</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>34</v>
+        <v>37.7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7311/1597</t>
+          <t>7311/1379</t>
         </is>
       </c>
     </row>
@@ -10021,94 +9910,96 @@
       <c r="C29" t="inlineStr">
         <is>
           <t># 全文摘要
-中共巢湖市银屏镇白母山村芦塘支部召开党员大会，改选支部委员会。支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。镇党委组织委员钱小丽到会讲话，就换届选举提出三点意见。大会依次通过上届支部委员会工作报告、党员大会选举办法草案、支委候选人名单（卢燕娇、辛东升、杜军强、秦磊）及监票人贾淑玲、计票人黄婷丽、刘彩云名单。
-上届支部委员会工作报告总结三年工作：新发展党员1名，收缴党费2640元上交上级党组织，开展两学一做学习教育常态化制度化及讲严例专题警示教育，通过党内会议、公开栏公开年度工作计划、党风廉政建设、党费收缴等内容；同时指出党建工作制度不够完善、党员主体意识尚需提高、党支部对党员教育管理监督不够深入三个问题。党员对报告无意见，鼓掌通过。
-四位候选人依次进行竞职演说。大会选举发出选票7张、收回7张，计票结果吴艳娇6票、杜军强6票、秦磊2票，吴艳娇、辛东升、杜军强当选为新一届支部委员会委员。随后召开第一次支部委员会全体会议，发出选票3张、收回3张，吴艳娇得3票当选为支部书记，并分工辛东升负责组织宣传工作、杜军强负责纪检工作。新当选支委代表吴艳娇发言，承诺抓好支部学习、制度建设和完善基层党组织建设，大会圆满结束。
+中共巢湖市银屏镇白母山村芦塘支部召开党员大会改选支部委员会，支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数；镇党委组织委员钱小丽到会讲话。会议围绕换届选举展开，依次通过选举办法、支委候选人名单、监票计票人员名单，听取四位候选人竞职演说，经无记名投票选举产生新一届支部委员和书记，并完成委员分工。最终吴艳娇、辛东升、杜军强当选支部委员，吴艳娇以3票当选支部书记，辛东升负责组织宣传、杜军强负责纪检；上届工作报告总结三年工作并指出存在问题，经审议通过。关键数字：党员8名、实到7名、党费2640元、委员候选人4名、吴艳娇获6票。
 # 分段速览
 ## 00:00:13-00:02:03 大会开幕
-主持人吴艳娇宣布会议开始，说明支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。镇党委组织委员钱小丽应邀到会，全体起立奏国歌。
+主持人宣布中共巢湖市银屏镇白母山村芦塘支部党员大会开始，报告支部共有党员8名、正式党员8名且有选举权，因病请假1名，实到有选举权党员7名，符合法定人数。全体起立奏国歌后，主持人邀请镇党委组织委员钱小丽讲话。
 ## 00:02:15-00:02:41 镇党委讲话
-钱小丽代表镇党委就换届选举提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律，并希望新一届班子加强学习、发挥战斗堡垒作用。
+钱小丽代表镇党委就换届选举提出三点意见：充分认识大会重要意义、正确行使选举权并严格把握选举要求、服从大局严格遵守选举纪律。她希望新一届班子加强学习、提高素质、发挥战斗堡垒作用，带领全村党员群众将村建设得更加美好。
 ## 00:02:41-00:05:12 上届支部委员会工作报告
-吴艳娇代表上届支部委员会作三年工作报告，从思想政治建设、支部建设、主题教育活动、党务公开、党风党纪教育五个方面总结成绩，同时指出党建工作制度不够完善、党员主体意识尚需提高、党员教育管理监督不够深入三个问题。党员对报告无意见，鼓掌通过。
+主持人代表上届支部委员会作三年工作报告，从思想政治建设、支部凝聚力、主题教育活动、党务公开、党风党纪教育五个方面总结成绩，同时指出党建工作制度不够完善、党员主体意识尚需提高、对党员教育管理监督不够深入等问题。报告经讨论无意见，鼓掌通过。
 ## 00:05:55-00:08:39 通过大会选举办法
-杜军晓宣读党员大会选举办法草案，规定选举委员3名、候选人4名，差额不少于应选名额20%，采用无记名投票，先差额选委员再等额选书记。党员举手表决一致通过。
-## 00:08:39-00:10:43 通过候选人及工作人员名单
-杜军晓宣读镇党委批复，委员候选人预备人选为卢燕娇、辛东升、杜军强、秦磊，书记候选人预备人选为卢艳娇，批复日期2019年10月12日。候选人名单经鼓掌通过，贾淑玲经举手表决担任监票人，计票人为黄婷丽、刘彩云。
+杜军晓宣读党员大会选举办法草案，规定选举支部委员3名、候选人4名，差额不少于应选名额20%，采用无记名投票，先差额选委员再等额选书记，实到有选举权党员须超过应到4/5方可选举，候选人得赞成票超过实到会选举人数半数方可当选。经举手表决一致通过。
+## 00:09:09-00:10:43 通过候选人及工作人员名单
+杜军晓宣读镇党委2019年10月12日批复，同意委员候选人预备人选4名（卢燕娇、辛东升、杜军强、秦磊），书记候选人预备人选卢艳娇，委员差额选举差额1人、书记等额选举。名单鼓掌通过。提议贾淑玲任监票人，表决通过；宣布计票人员黄婷丽、刘彩云。
 ## 00:10:43-00:14:45 候选人竞职演说
-四位候选人依次演说。吴艳娇承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强表示可更好担当主带角色；辛东升承诺群众需要到哪里去哪里、严格要求自己；秦磊阐述有责任心、思想觉悟高等有利条件。
+四位候选人依次发表竞职演说。吴艳娇介绍自己1993年9月出生、2014年4月入党，承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强介绍从事村委会工作，承诺担当主带角色服务党员群众；辛东升承诺群众需要到哪里就去哪里、严格要求自己、完成上级任务；秦磊介绍自己有责任心和思想觉悟，承诺配合上级工作当合格支部委员。
 ## 00:14:45-00:21:17 大会选举支部委员
-清点人数确认实到7名，达到应到会选举权党员人数的4/5。发出选票7张、收回7张，选举有效。计票结果：吴艳娇6票、杜军强6票、秦磊2票。吴艳娇、辛东升、杜军强当选为新一届支部委员会委员。
-## 00:21:17-00:28:42 第一次支委会选举书记及分工
-召开第一次支部委员会全体会议，宣读选举办法草案，介绍书记候选人建议名单，金东升经表决担任监票人和计票人。发出选票3张、收回3张，吴艳娇得3票当选为支部书记，分工辛东升负责组织宣传工作、杜军强负责纪检工作。
-## 00:28:42-00:29:56 新当选代表发言及大会闭幕
-吴艳娇代表新当选委员发言，承诺抓好支部学习工作、制度建设工作，完善基层党组织建设，争创学习型、制度型、服务型支部。大会宣布换届选举圆满结束，全体起立奏国际歌。
+清点人数确认实到有选举权党员7名、达到4/5，检查封好票箱后分发选票并说明填写方法。发出选票7张、收回7张，选举有效。计票结果：吴艳娇6票、杜军强6票、秦磊2票。吴艳娇、辛东升、杜军强当选为新一届支部委员会委员。
+## 00:21:17-00:27:55 第一次支委会选举书记及分工
+召开第一次支部委员会全体会议，宣读选举办法草案，通过吴艳娇为书记候选人建议名单，金东升任监票人和计票人。发出选票3张、收回3张，吴艳娇3票当选支部书记。分工：辛东升负责组织宣传工作，杜军强负责纪检工作。
+## 00:27:55-00:29:56 大会闭幕
+主持人宣布吴艳娇当选支部书记，结果以报镇党委批准为准。新当选支委代表发言，承诺抓好支部学习、制度建设和完善基层党组织建设，争创学习型、制度型、服务型支部。大会完成各项任务后圆满结束，全体起立奏国际歌。
 # 要点梳理
-## 会议开场与镇党委讲话
-- **会议合法性确认**：支部共有党员8名，其中正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数，可以开会。
-- **参会人员**：银屏镇党委组织委员钱小丽应邀到会，会议宣布开始后全体起立奏国歌。
-- **钱小丽讲话**：代表镇党委就换届选举提三点意见——充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律；希望新一届班子加强学习、提高素质，发挥战斗堡垒作用。
+## 换届选举大会开幕及镇党委讲话
+- **党员人数**：支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到有选举权党员7名，符合法定人数，可以开会。
+- **参会领导**：银屏镇党委组织委员钱小丽应邀参加，主持人宣布大会开始并奏国歌。
+- **钱小丽讲话**：代表镇党委就换届选举提三点意见——充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。
+- **对班子期望**：希望新一届班子加强学习、提高素质、发挥战斗堡垒作用，带领全村党员和群众将白母山村建设得更加美好。
 ## 上届支部委员会工作报告
-- **三年工作总结**：在上级党组织领导下，团结带领支部全体党员，认真落实党建工作各项要求，努力打造团结向上的先进集体。
+- **三年工作总结**：卢塘党支部在上级党组织领导和关怀下，认真落实党建工作各项要求，发挥党支部战斗堡垒作用和党员模范带头作用。
 - **思想政治建设**：大力加强思想政治建设和理论学习，努力提高党员干部的思想理论水平。
-- **支部建设**：严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度；新发展党员1名。
-- **党费收缴**：按规定收缴党费2640元上交上级党组织。
-- **主题教育活动**：认真开展两学一做学习教育常态化、制度化和讲严例专题警示教育活动。
-- **党务公开**：将年度工作计划、党风廉政建设、党费收缴等内容，通过党内会议、公开栏等形式进行公开。
-- **党风党纪教育**：认真抓好党风党纪教育，筑牢拒腐防变的思想防线，党风廉政建设的各项责任落到实处。
-- **存在问题**：一是党建工作制度不够完善；二是党员主体意识尚需进一步提高，个别党员干部顶推中心服务大局的意识还不强；三是党支部对党员的教育管理监督还不够深入。
-- **报告审议**：党员对工作报告无意见，鼓掌通过。
+- **支部建设**：严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度；新发展党员1名，按规定收缴党费2640元上交上级党组织。
+- **主题教育活动**：认真开展“两学一做”学习教育常态化、制度化和“讲严例”专题警示教育活动。
+- **党务公开**：将年度工作计划、党风廉政建设、党费收缴等内容通过党内会议、公开栏等形式公开。
+- **党风党纪教育**：认真抓好党风党纪教育，筑牢拒腐防变思想防线，落实党风廉政建设各项责任。
+- **存在问题**：一是党建工作制度不够完善；二是党员主体意识尚需提高，个别党员干部围绕中心服务大局意识不强；三是党支部对党员教育管理监督不够深入。
+- **报告审议**：经讨论无意见，鼓掌通过。
 ## 通过大会选举办法
-- **选举办法要点**：选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；候选人按姓氏笔画为序排列，采用无记名投票方式。
-- **选举步骤**：先差额选举支部委员会委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布选举结果。
-- **有效条件**：参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；收回选票数等于或少于发出选票数选举有效，多于则无效。
-- **当选规则**：候选人得到赞成票数超过实到会选举人数的半数方可当选；得票超过半数的候选人多于应选名额时以得票多少为序取足；最后几名得票相等时重新投票。
-- **不足名额处理**：得票超过半数的候选人少于应选名额时，不足名额在未超过半数候选人中重新选举产生，接近应选名额可减少名额不再选举。
-- **选票填写**：投赞成票在候选人姓名上方空格画圈，不赞成画叉，弃权不画符号；另选他人需写姓名并画圈；每张选票所选人数等于或少于应选人数有效，超过无效。
-- **工作人员设置**：设监票人1名，经大会表决通过；设选举工作人员2名，由会议主持人指定；候选人不能担任监票人和工作人员。
-- **表决结果**：党员无不同意见，举手表决一致通过选举办法草案。
+- **选举办法要点**：选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；候选人按姓氏笔画为序排列；采用无记名投票方式。
+- **选举程序**：先差额选举支部委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布结果。
+- **有效条件**：参加会议有选举权的正式党员必须超过应到会党员的4/5方可选举；收回选票等于或少于发出选票选举有效，多于则无效。
+- **当选规则**：候选人得赞成票超过实到会选举人数半数方可当选；得票超过半数的候选人多于应选名额时按得票多少取足；最后几名得票相等时重新投票。
+- **选票填写**：赞成画圈、不赞成画叉、弃权不画；另选他人需写姓名并画圈；每张选票所选人数等于或少于应选人数有效，超过无效。
+- **表决结果**：杜军晓宣读选举办法草案，经举手表决一致通过。
 ## 通过支委候选人名单
-- **镇党委批复**：银屏镇党委批复同意新一届支部委员会委员和书记候选人预备人选名单，批复日期2019年10月12日。
-- **委员候选人**：卢燕娇、辛东升、杜军强、秦磊4名，委员实行差额选举，差额1人。
-- **书记候选人**：卢艳娇，实行等额选举。
-- **表决结果**：党员无不同意见，鼓掌通过候选人名单。
+- **镇党委批复**：杜军晓宣读银屏镇党委批复，同意新一届支部委员会委员和书记候选人预备人选名单，批复日期2019年10月12日。
+- **候选人名单**：委员候选人预备人选4名——卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢艳娇。
+- **选举方式**：委员实行差额选举，差额1人；书记实行等额选举。
+- **表决结果**：无不同意见，鼓掌通过。
 ## 通过选举工作人员名单
-- **监票人**：提议贾淑玲担任监票人，经举手表决一致通过。
-- **计票人**：宣布黄婷丽、刘彩云为计票人员。
+- **监票人**：提议贾淑玲同志担任监票人，经举手表决一致通过。
+- **计票人员**：宣布黄婷丽、刘彩云为计票人员。
 ## 候选人竞职演说
-- **吴艳娇**：1993年9月出生，2014年4月加入中国共产党；承诺进一步加强支部建设，落实三会一课、组织生活会和民主评议党员等基本制度，结合两学一做学习教育常态化制度化开展不忘初心、牢记使命主题教育；进一步推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领作用；进一步抓好各项民生工程落实，把群众利益作为工作首要职责。
-- **杜军强**：从事村委会工作，平时与各类人群有工作接触；承诺如果成为支部委员，可以更好担当主带角色，为党员和群众服务。
+- **吴艳娇**：1993年9月出生，2014年4月加入中国共产党；承诺加强支部建设、落实“三会一课”等制度，推动村集体经济发展，抓好民生工程，把群众满意度作为衡量工作标准。
+- **杜军强**：从事村委会工作，与各类人群有工作接触；承诺担当主带角色，为党员和群众服务。
 - **辛东升**：承诺群众需要到哪里去哪里，群众有困难随叫随到；严格要求自己做合格党员干部，不该吃的饭不吃、不该拿的钱不拿、不该做的事不做；圆满完成上级党组织分配的各项任务。
-- **秦磊**：竞选有利条件为有较强责任心、能认真参加支部组织的理论学习、有较高思想觉悟；承诺热情为群众办实事，配合上级各项工作，全体党员团结一心，不计较个人得失，当一名合格的支部委员。
-## 大会选举新一届支部委员会委员
-- **人数清点**：应到会有选举权党员8名，因病请假1名，实到7名，达到应到会选举权党员人数的4/5，可以进行选举。
-- **选举过程**：监票人员检查并封好票箱，领取并分发选票，说明填写方法后党员填写并依次投票。
-- **计票结果**：发出选票7张，收回选票7张，选举有效；计票结果吴艳娇6票、杜军强6票、秦磊2票。
-- **当选结果**：根据大会选举办法规定，吴艳娇、辛东升、杜军强当选为新一届支部委员会委员。
-## 第一次支部委员会全体会议选举书记及分工
-- **选举办法**：选举产生支部书记1人，采用等额选举办法；实到会委员必须超过应到会委员的4/5方可进行选举；候选人得到赞成票超过实到会委员的半数当选。
-- **书记候选人介绍**：吴艳娇同志工作认真负责，上届支委会在她的带领下各项工作都取得较好成绩，建议继续由吴艳娇担任支部书记，经鼓掌通过。
-- **监票人**：提议辛东升担任监票人和计票人，经举手表决一致通过。
-- **选举结果**：发出选票3张，收回选票3张，吴艳娇得3票，当选为新一届党支部书记。
+- **秦磊**：自述有较强责任心、能认真参加理论学习并完成组织任务，有较高思想觉悟；承诺配合上级工作、全体党员团结一心、不计较个人得失，当一名合格支部委员。
+## 大会选举支部委员
+- **人数清点**：应到会有选举权党员8名，因公请假1名，实到7名，达到应到会选举权党员人数的4/5，可以进行选举。
+- **选举过程**：监票人员检查并封好票箱，分发选票，说明填写方法后党员填写并依次投票。
+- **计票结果**：发出选票7张，收回选票7张，选举有效；计票结果——吴艳娇6票、杜军强6票、秦磊2票。
+- **选举结果**：吴艳娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。
+## 第一次支委会选举书记及分工
+- **选举办法**：选举产生支部书记1人，采用等额选举；实到会委员必须超过应到会委员的4/5方可选举；设监票人1名，由主持人在非书记候选人中提名。
+- **书记候选人**：介绍吴艳娇同志工作认真负责，上届支委会在其带领下各项工作取得较好成绩，建议继续由吴艳娇担任支部书记，无不同意见，鼓掌通过。
+- **工作人员**：提议辛东升担任监票人和计票人，经举手表决一致通过。
+- **选举结果**：发出选票3张，收回选票3张，吴艳娇3票当选为新一届党支部书记。
+- **委员分工**：辛东升负责组织宣传工作，杜军强负责纪检工作，无意见后明确。
+## 大会闭幕及新当选代表发言
+- **宣布结果**：主持人宣布吴艳娇当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。
+- **新当选代表发言**：代表新当选三位支部委员感谢信任，承诺抓好支部学习工作、争创学习型支部，抓好制度建设工作、争创制度型支部，完善基层党组织建设、争创服务型支部。
+- **大会结束**：宣布换届选举大会圆满结束，全体起立奏国际歌。
+## 结论与决定
+- **通过选举办法**：党员大会选举办法草案经举手表决一致通过。
+- **通过候选人名单**：支委候选人名单（卢燕娇、辛东升、杜军强、秦磊）经鼓掌通过，书记候选人吴艳娇经鼓掌通过。
+- **通过工作人员**：监票人贾淑玲、计票人员黄婷丽和刘彩云经表决通过。
+- **支部委员选举结果**：吴艳娇、辛东升、杜军强当选为新一届支部委员会委员。
+- **书记选举结果**：吴艳娇当选为支部书记，最终结果以报镇党委批准为准。
 - **委员分工**：辛东升负责组织宣传工作，杜军强负责纪检工作。
-## 新当选支委代表发言及大会闭幕
-- **吴艳娇代表发言**：代表新当选的三位支部委员感谢信任和支持；承诺抓好支部学习工作，争创学习型支部，认真组织开展不忘初心、牢记使命主题教育；抓好支部制度建设工作，争创制度型支部，增强党支部凝聚力、战斗力；完善基层党组织建设，争创服务型支部，严格按照中国共产党党支部工作条例（试行）加强支部建设，发挥战斗堡垒和党员先锋模范作用，更好服务基层服务群众。
-- **大会闭幕**：宣布换届选举大会圆满结束，全体起立奏国际歌。
-## 结论与决定
-- **通过上届支部委员会工作报告**：党员对报告无意见，鼓掌通过。
-- **通过党员大会选举办法草案**：经举手表决一致通过。
-- **通过支委候选人名单**：卢燕娇、辛东升、杜军强、秦磊，经鼓掌通过。
-- **通过监票人贾淑玲**，计票人黄婷丽、刘彩云，经举手表决一致通过。
-- **选举结果**：吴艳娇、辛东升、杜军强当选为新一届支部委员会委员；吴艳娇当选为支部书记，最终结果以报镇党委批准为准。
-- **委员分工**：辛东升负责组织宣传工作，杜军强负责纪检工作。</t>
+## 行动项与分工
+- **辛东升**：负责新一届支部组织宣传工作。
+- **杜军强**：负责新一届支部纪检工作。
+- **吴艳娇**：主持支部全面工作，承诺加强支部建设、推动村集体经济发展、抓好民生工程。
+- **选举结果上报**：选举结果报镇党委批准。</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>65.7</v>
+        <v>66.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8414/4574</t>
+          <t>8414/4379</t>
         </is>
       </c>
     </row>
@@ -10245,124 +10136,131 @@
       <c r="C30" t="inlineStr">
         <is>
           <t># 报告概况
-国务院总理代表国务院向十四届全国人大二次会议作政府工作报告，报告回顾2023年工作，提出2024年经济社会发展总体要求、政策取向和主要任务，请大会审议并请全国政协委员提出意见。报告指出，2023年国内生产总值超过**126万亿元**，增长**5.2%**，城镇新增就业1244万人，居民消费价格上涨0.2%，粮食产量1.39万亿斤，新能源汽车产销量占全球比重超过60%，可再生能源发电装机历史性超过火电，全年经济社会发展主要目标任务圆满完成。
-报告分析了当前面临的困难和挑战：外部环境复杂性、严峻性、不确定性上升，经济持续回升向好的基础还不稳固，有效需求不足，社会预期偏弱，风险隐患仍然较多，部分中小企业经营困难，就业总量压力和结构性矛盾并存，安全生产薄弱环节不容忽视，政府工作存在形式主义、官僚主义现象，一些领域腐败问题仍然多发。
-报告提出2024年主要预期目标：国内生产总值增长**5%左右**，城镇新增就业1120万人以上，城镇调查失业率5.5%左右，居民消费价格涨幅3%左右，居民收入增长和经济增长同步，粮食产量1.3万亿斤以上，单位国内生产总值能耗降低2.5%左右。宏观政策上，赤字率拟按3%安排，赤字规模4.06万亿元，一般公共预算支出规模28.5万亿元，拟安排地方政府专项债券3.9万亿元，今年先发行10000亿元超长期特别国债，稳健的货币政策要灵活适度、精准有效。
-报告部署2024年政府工作任务，涵盖大力推进现代化产业体系建设、加快发展新质生产力，深入实施科教兴国战略，着力扩大国内需求，坚定不移深化改革，扩大高水平对外开放，更好统筹发展和安全，坚持不懈抓好三农工作，加强生态文明建设，切实保障和改善民生等十个方面。
+国务院总理代表国务院向十四届全国人大二次会议作政府工作报告，报告期间覆盖2023年工作回顾与2024年工作部署。报告回顾2023年经济社会发展成绩：国内生产总值超过126万亿元、增长5.2%，城镇新增就业1244万人，粮食产量1.39万亿斤再创历史新高，可再生能源发电装机规模历史性超过火电，全年经济社会发展主要目标任务圆满完成。报告同时指出面临的困难和挑战，包括外部环境复杂性上升、有效需求不足、社会预期偏弱、部分中小企业经营困难等。2024年主要预期目标为国内生产总值增长5%左右、城镇新增就业1120万人以上、城镇调查失业率5.5%左右、居民消费价格涨幅3%左右、粮食产量1.3万亿斤以上；赤字率拟按3%安排，一般公共预算支出规模28.5万亿元，拟安排地方政府专项债券3.9万亿元，今年先发行10000亿元超长期特别国债。报告部署2024年政府工作十项任务，涵盖现代化产业体系建设、科教兴国、扩大内需、深化改革、对外开放、统筹发展和安全、三农工作、城乡区域协调、生态文明建设、民生保障等方面，并强调坚持稳中求进工作总基调，巩固和增强经济回升向好态势，以中国式现代化全面推进强国建设、民族复兴伟业。
 # 核心政策
-- **总体要求**：坚持稳中求进、以进促稳、先立后破，完整、准确、全面贯彻新发展理念，加快构建新发展格局，着力推动高质量发展，统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全，持续推动经济实现质的有效提升和量的合理增长。
-- **政策取向**：多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施；强化宏观政策逆周期和跨周期调节，把非经济性政策纳入宏观政策取向一致性评估，确保同向发力、形成合力；涉企政策注重与市场沟通，回应企业关切，营造稳定、透明、可预期的政策环境。
-**2024年主要预期目标**：
-- **国内生产总值增长5%左右**。
-- **城镇新增就业1120万人以上**，城镇调查失业率5.5%左右。
-- **居民消费价格涨幅3%左右**。
-- 居民收入增长和经济增长同步，国际收支保持基本平衡。
-- **粮食产量1.3万亿斤以上**。
-- **单位国内生产总值能耗降低2.5%左右**，生态环境质量持续改善。
-**财政政策**：
-- 积极的财政政策适度加力、提质增效，赤字率拟按3%安排，赤字规模4.06万亿元，一般公共预算支出规模28.5万亿元。
-- 拟安排地方政府专项债券3.9万亿元；为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，今年先发行10000亿元。
-- 大力优化支出结构，强化国家重大战略任务和基本民生财力保障；中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜，省级财政推动财力下沉，兜牢基层`三保`底线；各级政府要习惯过紧日子，把财政资金用在刀刃上。
-**货币政策**：
-- 稳健的货币政策灵活适度、精准有效，保持流动性合理充裕，社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配。
-- 促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。
-**现代化产业体系建设**：
-- 实施`制造业重点产业链高质量发展`行动，着力补齐短板、拉长长板、锻造新板，推动传统产业高端化、智能化、绿色化转型，促进中小企业专精特新发展，打造更多有影响力的中国制造品牌。
-- 促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
-- 深入推进数字经济创新发展，制定支持数字经济高质量发展政策，开展`人工智能+`行动，实施`制造业数字化转型`行动，大力推动数据开发开放和流通使用。
-**科教兴国战略**：
-- 制定实施`教育强国建设规划纲要`，开展`基础教育扩优提质`行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
-- 充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研究，强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革。
-- 实施更加积极、更加开放、更加有效的人才政策，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
-**扩大内需**：
-- 促进消费稳定增长，从增加收入、优化供给、减少限制性措施等方面综合施策，实施数字消费、绿色消费、健康消费促进政策，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大众消费，推动养老、育幼、家政等服务扩容提质。
-- 积极扩大有效投资，发挥政府投资带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳，加快实施`十四五`规划重大工程项目，着力稳定扩大民间投资，在更多领域让民间投资进得来、能发展、有作为。
-**深化改革**：
-- 不断完善落实`两个毫不动摇`的体制机制，深入实施`国有企业改革深化提升`行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制。
-- 加快全国统一大市场建设，着力推动产权保护、市场准入、公平竞争、社会信用等方面制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题。
-- 谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
-**高水平对外开放**：
-- 推动外贸稳规模优结构，支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，出台服务贸易、数字贸易创新发展政策。
-- **全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，深入实施`自贸试验区提升`战略。
-- 推动高质量共建`一带一路`走深走实，抓好支持高质量共建`一带一路`八项行动落实落地，稳步推进重大项目合作，实施一批`小而美`民生项目，加快建设西部陆海新通道。
-**统筹发展和安全**：
-- 优化房地产政策，促进房地产市场平稳健康发展，加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求。
-- 统筹好地方债务风险化解和稳定发展，进一步落实`一揽子化债方案`，稳妥推进一些地方的中小金融机构风险处置，建立同高质量发展相适应的政府债务管理机制。
-- 全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
-**乡村全面振兴**：
-- 学习运用`千村示范、万村整治`工程经验，稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平。
-- 毫不放松巩固拓展脱贫攻坚成果，加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度。
-- **启动第二轮土地承包到期后再延长30年整省试点**，深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
-**新型城镇化和区域协调**：
-- 把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，推动未落户常住人口平等享受城镇基本公共服务。
-- 深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展。
-**生态文明建设**：
-- 深入践行`绿水青山就是金山银山`理念，协同推进降碳、减污、扩绿、增长，深入实施`空气质量持续改善行动计划`，统筹水资源、水环境、水生态治理，组织打好`三北`工程三大标志性战役。
-- 大力发展绿色低碳经济，推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，推动废弃物循环利用产业发展，建设美丽中国先行区。
-- 积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系。
-**民生保障**：
-- 突出就业优先导向，预计今年高校毕业生超过1170万人，强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作，多渠道增加城乡居民收入，扩大中等收入群体规模。
-- **居民医保人均财政补助标准提高30元**，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新。
-- **城乡居民基础养老金月最低标准提高20元**，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担，健全分层分类的社会救助体系。
+**发展目标与总体要求**
+- **总体基调**：坚持`稳中求进、以进促稳、先立后破`，多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施；统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全。
+- **2024年主要预期目标**：国内生产总值增长**5%左右**；城镇新增就业**1120万人以上**；城镇调查失业率**5.5%左右**；居民消费价格涨幅**3%左右**；居民收入增长和经济增长同步；国际收支保持基本平衡；粮食产量**1.3万亿斤以上**；单位国内生产总值能耗降低**2.5%左右**。
+- **形势判断**：今年我国发展面临的环境仍是战略机遇和风险挑战并存，**有利条件强于不利因素**；实现今年预期目标并非易事，需要政策聚焦发力、工作加倍努力、各方面齐心协力。
+**宏观政策取向**
+- **积极的财政政策**：要`适度加力、提质增效`；赤字率拟按**3%**安排，一般公共预算支出规模**28.5万亿元**；拟安排地方政府专项债券**3.9万亿元**。
+- **超长期特别国债**：为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，**今年先发行10000亿元**。
+- **财政支出结构**：大力优化支出结构，强化国家重大战略任务和基本民生财力保障；中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜；省级财政推动财力下沉，兜牢基层`三保`底线；各级政府要习惯过紧日子。
+- **稳健的货币政策**：要`灵活适度、精准有效`，保持流动性合理充裕；社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配；促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。
+- **宏观政策取向一致性**：围绕发展大局加强政策协调配合，**把非经济性政策纳入宏观政策取向一致性评估**，确保同向发力、形成合力；涉企政策要注重与市场沟通，回应企业关切，营造稳定、透明、可预期的政策环境。
+**产业与创新政策**
+- **现代化产业体系建设**：实施`制造业重点产业链高质量发展行动`，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型；促进中小企业`专精特新`发展；巩固扩大智能网联、新能源汽车等产业领先优势；制定未来产业发展规划，鼓励发展创业投资、股权投资。
+- **数字经济**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合；开展`人工智能+`行动；实施`制造业数字化转型行动`；大力推动数据开发开放和流通使用。
+- **科教兴国**：制定实施`教育强国建设规划纲要`，开展`基础教育扩优提质行动`；充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关；强化企业科技创新主体地位；实施更加积极、更加开放、更加有效的人才政策，加大对青年科技人才支持力度。
+**内需与开放政策**
+- **扩大国内需求**：从增加收入、优化供给、减少限制性措施等方面综合施策促进消费稳定增长；实施数字消费、绿色消费、健康消费促进政策；鼓励和推动消费品以旧换新；发挥政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳等领域；着力稳定扩大民间投资。
+- **深化改革**：深入实施`国有企业改革深化提升行动`；全面落实促进民营经济发展壮大的意见及配套举措；实施`降低物流成本行动`，健全防范化解拖欠企业账款长效机制；加快全国统一大市场建设，专项治理地方保护、市场分割、招商引资不当竞争等突出问题；谋划新一轮财税体制改革。
+- **高水平对外开放**：推动外贸`稳规模、优结构`，促进跨境电商等新业态健康发展；**全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入；深入实施`自贸试验区提升战略`；抓好支持高质量共建`一带一路`八项行动落实落地。
+**安全与民生政策**
+- **防范化解重点领域风险**：优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实`一揽子化债方案`；稳妥推进中小金融机构风险处置；加快构建房地产发展新模式，加大保障性住房建设和供给。
+- **三农与乡村振兴**：学习运用`千村示范、万村整治`工程经验；稳定粮食播种面积，严守耕地红线，提高高标准农田建设投资补助水平；确保不发生规模性返贫；**启动第二轮土地承包到期后再延长30年整省试点**。
+- **新型城镇化与区域协调**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革；深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用。
+- **生态文明建设**：深入实施`空气质量持续改善行动计划`；组织打好`三北`工程三大标志性战役；扎实开展`碳达峰十大行动`，加快建设新型能源体系。
+- **就业与收入**：突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过**1170万人**，要强化促进青年就业政策；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
+- **医疗与社保**：居民医保人均财政补助标准**提高30元**；深化公立医院改革，引导优质医疗资源下沉基层；城乡居民基础养老金月最低标准**提高20元**，继续提高退休人员基本养老金；健全生育支持政策，减轻家庭生育养育教育负担。
 # 重点工作
 ## 现代化产业体系建设
-- **推动产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板，推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌。
-- **战略性新兴产业融合集群发展**：巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
-- **数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展“人工智能+”行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
+- **产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板。
+- **传统产业转型**：推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展。
+- **品牌建设**：加强标准引领和质量支撑，打造更多有影响力的中国制造品牌。
+- **战略性新兴产业**：促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势。
+- **未来产业布局**：制定未来产业发展规划，鼓励发展创业投资、股权投资。
+- **数字经济创新**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展“人工智能+”行动。
+- **数字化转型**：实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
 ## 科教兴国战略
-- **高质量教育体系建设**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务，开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
-- **高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发，强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作。
-- **人才培养**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
+- **高质量教育体系**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务。
+- **基础教育扩优提质**：开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量。
+- **高等教育建设**：加快建设中国特色世界一流的大学和优势学科。
+- **科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发。
+- **企业创新主体**：强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护。
+- **开放创新生态**：扩大国际科技交流合作，营造具有全球竞争力的开放创新生态。
+- **人才政策**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度。
+- **人才评价改革**：加快建立以创造价值、能力、贡献为导向的人才评价体系。
 ## 扩大国内需求
-- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策，稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大众消费，推动养老、育幼、家政等服务扩容提质。
-- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳，加强民生等经济社会薄弱领域，加快实施“十四五”规划重大工程项目，着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，让民间投资进得来、能发展、有作为。
+- **消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策。
+- **以旧换新**：稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大众消费。
+- **服务消费扩容**：推动养老、育幼、家政等服务扩容提质，优化消费环境。
+- **有效投资**：发挥政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域。
+- **重大工程项目**：加快实施“十四五”规划重大工程项目。
+- **民间投资**：着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
 ## 深化改革
-- **激发各类经营主体活力**：不断完善落实“两个毫不动摇”的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境，深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制。
-- **全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
-- **财税金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
-## 扩大高水平对外开放
-- **推动外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
-- **加大吸引外资力度**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施自贸试验区提升战略，打造对外开放新高地。
-- **高质量共建“一带一路”**：抓好支持高质量共建“一带一路”八项行动落实落地，稳步推进重大项目合作，实施一批“小而美”民生项目，加快建设西部陆海新通道。
-- **深化多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
+- **经营主体活力**：不断完善落实“两个毫不动摇”的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境。
+- **国企改革**：深入实施国有企业改革深化提升行动。
+- **民营经济**：全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制。
+- **企业家支持**：积极支持企业家专注创新发展，敢干、敢闯、敢投，踏踏实实把企业办好。
+- **全国统一大市场**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题。
+- **财税金融改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
+## 高水平对外开放
+- **外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口。
+- **服务贸易与数字贸易**：出台服务贸易、数字贸易创新发展政策。
+- **吸引外资**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障。
+- **自贸试验区**：深入实施自贸试验区提升战略，打造对外开放新高地。
+- **共建“一带一路”**：抓好支持高质量共建“一带一路”八项行动落实落地，稳步推进重大项目合作，实施一批“小而美”民生项目，加快建设西部陆海新通道。
+- **多双边合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
 ## 统筹发展和安全
-- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任，优化房地产政策，促进房地产市场平稳健康发展，统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
-- **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求，建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
-- **重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
+- **风险隐患处置**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任。
+- **房地产政策**：优化房地产政策，促进房地产市场平稳健康发展，加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求。
+- **地方债务化解**：统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
+- **风险防控长效机制**：建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
+- **粮食安全**：全方位夯实粮食安全根基。
+- **能源资源安全**：强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
 ## 三农工作与乡村全面振兴
-- **粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平。各地区都要扛起保障国家粮食安全责任。
-- **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
-- **农村改革发展**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业，深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
-## 城乡融合和区域协调发展
+- **稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平。
+- **粮食安全责任**：各地区都要扛起保障国家粮食安全责任。
+&gt; 我们这样一个人口大国，必须始终把饭碗牢牢端在自己手上。
+- **巩固脱贫成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度。
+- **农村改革**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业。
+- **乡村建设**：深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
+## 城乡融合与区域协调发展
 - **新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
-- **区域协调发展**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
+- **以人为本**：新型城镇化要处处体现以人为本，让人民群众享有更高品质的生活。
+- **区域战略**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略。
+- **动力源作用**：支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展。
+- **主体功能区**：制定主体功能区优化实施规划。
 ## 生态文明建设
-- **生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好“三北”工程三大标志性战役，完善生态产品价值实现机制。
-- **绿色低碳经济发展**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
+- **生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控。
+- **三北工程**：组织打好“三北”工程三大标志性战役。
+- **生态产品价值实现**：完善生态产品价值实现机制，充分调动各方面保护和改善生态环境的积极性。
+- **绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链。
+- **美丽中国先行区**：建设美丽中国先行区。
 - **碳达峰碳中和**：扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
-## 保障和改善民生
-- **稳就业促增收**：突出就业优先导向，加大促就业专项政策力度。预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作，多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
-- **提高医疗卫生服务能力**：居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展健康中国行动和爱国卫生运动。
-- **加强社会保障**：城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担，健全分层分类的社会救助体系。
-- **丰富精神文化生活**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。
-- **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生，完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代“枫桥经验”，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动。
+## 民生保障和社会治理
+- **稳就业促增收**：突出就业优先导向，加大促就业专项政策力度，预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作。
+- **居民增收**：多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
+- **医疗卫生**：居民医保人均财政补助标准提高**30元**，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新。
+- **健康中国**：深入开展健康中国行动和爱国卫生运动，筑牢人民群众健康防线。
+- **社会保障**：城乡居民基础养老金月最低标准提高**20元**，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设。
+- **生育支持**：健全生育支持政策，减轻家庭生育养育教育负担。
+- **社会救助**：健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢。
+- **文化事业**：深入学习贯彻习近平文化思想，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。
+- **公共安全**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生。
+- **社会治理**：完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代“枫桥经验”，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动。
 ## 政府自身建设
-- **依法行政与监督**：深入推进依法行政，严格遵守宪法法律，自觉接受同级人大及其常委会的监督、人民政协的民主监督、社会和舆论监督，加强审计监督，坚持科学民主依法决策。
-- **提高行政效能**：深入推进政府职能转变，不断提高执行力和公信力，在抓落实上切实做到不折不扣、雷厉风行、求真务实，坚决纠正形式主义、官僚主义，持续为基层和企业减负。
-- **廉政建设**：发扬自我革命精神，纵深推进党风廉政建设和反腐败斗争，政府工作人员要遵守法纪、廉洁修身、勤勉尽责，干干净净为人民服务。
-## 国防、港澳台与外交
-- **国防和军队建设**：深入贯彻习近平强军思想，贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全面深入贯彻军委主席负责制，打好实现建军一百年奋斗目标攻坚战，全面加强练兵备战，抓好军队建设“十四五”规划执行，加快实施国防发展重大工程。
-- **港澳工作**：继续全面准确、坚定不移贯彻“一国两制”、“港人治港”、“澳人治澳”、高度自治的方针，坚持依法治港治澳，落实爱国者治港、爱国者治澳的原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局。
-- **对台工作**：坚持贯彻新时代党解决台湾问题的总体方略，坚持一个中国原则和“九二共识”，坚决反对“台独”分裂和外来干涉，推动两岸关系和平发展，深化两岸融合发展，增进两岸同胞福祉。
-- **外交工作**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体。</t>
+- **依法行政**：严格遵守宪法法律，自觉接受同级人大及其常委会的监督，自觉接受人民政协的民主监督，自觉接受社会和舆论监督，加强审计监督，坚持科学民主依法决策。
+- **廉政建设**：发扬自我革命精神，纵深推进党风廉政建设和反腐败斗争，政府工作人员要遵守法纪、廉洁修身、勤勉尽责。
+- **行政效能**：深入推进政府职能转变，不断提高执行力和公信力，在抓落实上切实做到不折不扣、雷厉风行、求真务实。
+- **纠治形式主义**：坚决纠正形式主义、官僚主义，持续为基层和企业减负。
+## 民族、宗教、国防与外交
+- **民族工作**：以铸牢中华民族共同体意识为主线，促进各民族广泛交往、交流、交融。
+- **宗教与侨务**：坚持党的宗教工作基本方针，深入推进我国宗教中国化，加强和改进侨务工作。
+- **国防和军队建设**：深入贯彻习近平强军思想，贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全面深入贯彻军委主席负责制，打好实现建军一百年奋斗目标攻坚战。
+- **练兵备战**：全面加强练兵备战，坚定捍卫国家主权、安全、发展利益，抓好军队建设“十四五”规划执行，加快实施国防发展重大工程。
+- **港澳工作**：继续全面准确、坚定不移贯彻“一国两制”、“港人治港”、“澳人治澳”、高度自治的方针，坚持依法治港治澳，落实爱国者治港、爱国者治澳原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局。
+- **台湾问题**：坚持贯彻新时代党解决台湾问题的总体方略，坚持一个中国原则和“九二共识”，坚决反对“台独”分裂和外来干涉，推动两岸关系和平发展，深化两岸融合发展。
+- **外交政策**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体。</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>59.8</v>
+        <v>72.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9903/7851</t>
+          <t>9903/7414</t>
         </is>
       </c>
     </row>
@@ -11197,93 +11095,93 @@
       <c r="C31" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-杭州医学院检验医学院、生物工程学院党委书记、副院长宋宝峰副教授做客直播间，面向B站、微博、抖音平台收看直播的考生及家长，介绍该校医学技术专业硕士点的总体情况。该学位点于2024年获批，由检验学院、生物工程学院（合署办公）牵头，联合医学影像学院、康复学院、信息工程学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向。宋宝峰系统介绍了学位点学科建设、科研平台、师资队伍、培养模式与就业去向，并重点解读2026年招考计划，包括初试科目、考试大纲、复试方式与占比。2025年该学位点已录取64名考生，2026年计划招生34人（以教育部正式下达为准）。直播后半段，宋宝峰就考生关心的就业前景、初试备考、跨专业报考等问题逐一解答，明确允许非本专业考生跨专业报考，整体基调为积极欢迎考生报考。
+杭州医学院检验医学院、生物工程学院党委书记宋宝峰副教授做客直播间，面向考生及家长介绍医学技术专业硕士点情况。该学位点于2024年获批，由检验医学院、生物工程学院（合署办公）牵头，联合医学影像学院、康复学院、信息工程学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向。2025年已录取64名考生，2026年计划招生34人（以教育部正式下达为准）。宋宝峰从学位点概况、学科优势、研究方向、师资队伍、培养与就业、招考计划等方面展开介绍，并解答了考生关于就业前景、初试科目、跨专业报考等关切问题，整体基调为积极推介，鼓励考生报考。
 # 核心信息与数据
 ## 学位点基本情况
-- **学位点获批**：医学技术专业硕士点于2024年获批，为新增学位点。
-- **学院构成**：由5个学院共同承担培养工作，组建学院为检验学院、生物工程学院（合署办公），共建学院为医学影像学院、康复学院、信息工程学院。
-- **专业方向**：聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向，其中检验技术细分为医检和卫检两个方向。
+- **学位点获批**：医学技术专业硕士点于2024年获批，由5个学院共同承担培养工作。
+- **学院构成**：组建学院为检验医学院、生物工程学院（合署办公），共建学院为医学影像学院、康复学院、信息工程学院。
+- **专业方向**：聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个主要方向，其中检验技术细分为医检和卫检两个方向。
 ## 2025年招生情况
-- **录取人数**：2025年录取64位考生，其中检验方向38人、经济方向11人、康复方向13人、职业方向24人。
+- **招生总数**：2025年录取64位考生，其中检验方向38人、经济方向11人、康复方向13人、职业方向24人。
 ## 学科建设与科研平台
-- **学科建设**：2023年获批省医学技术省一流学科B类；近五年获国家级基金项目19项、省鉴定领先项目1项。
+- **学科层次**：2023年获批省医学技术省一流学科B类。
+- **科研项目**：近五年获国家级基金项目19项、省鉴定领先项目1项。
 - **科研经费**：纵向科研经费1300万元，横向合作课题经费2200多万元。
-- **科研成果**：获省科技进步一等奖2项、二等奖1项、三等奖2项；建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
-- **省级平台**：建有省生物标志物与器官诊断转化重点实验室（今年获批）、检验诊断关键技术质量研究室（2022年）、康复模块和机器人国际联合实验室（2023年）、省实验室和安全培训基地、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心，以及2024年获批的浙江省神经系统疾病数字化装备研发重点实验室。
+- **科研成果**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
+- **教学建设**：建有国家级一流本科课程2门、国家级一流本科专业建设点2个。
+- **省级平台**：2024年获批省生物标志物与器官诊断转化重点实验室；2022年打造检验诊断关键技术质量研究室；2023年打造康复模块和机器人国际联合实验室、省实验室和安全培训基地、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心；2024年获批浙江省神经系统疾病数字化装备研发重点实验室。
 ## 学科优势
-- **体外诊断**：疫情期间联合企业开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册；是中华医学会检验医学分会教育学组组长单位、卫生高新技术公司实体开发基地。
-- **医学影像技术**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向，拥有国家级本科专业建设点、省医学重点学科、医学创新学科、省临床放射质控中心、省疾控中心国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地。
+- **体外诊断**：疫情期间联合企业开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册；是中华医学会检验分会教育学组组长单位、卫生高新技术公司实体开发基地。
+- **医学影像技术**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向；拥有国家级本科专业建设点、省医学重点学科、省医学创新学科、省临床放射质控中心、国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地等平台。
 - **康复治疗**：依托省人民医院康复医学科，为省内综合医院中建科最早、人才最齐、技术最先进、设备最先进、社会效益最佳的康复医学科之一。
-- **智能医学工程**：聚焦阿尔茨海默病智能预警生物标志物（数字生物标志物），居国际领跑水平；为浙江省中医药重点学科、老年助浴疾病数字医疗器械浙江省中心、智能医学前沿交叉学院。
+- **智能医学工程**：聚焦阿尔茨海默病智能预警数字生物标志物，居国际领跑水平；是浙江省中医药重点学科、老年助浴疾病数字医疗器械浙江省中心、智能医学前沿交叉学院。
 ## 主要研究方向
-- **医学检验技术**：负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制研究、新发突发传染病新型生物标志物筛选及致病机制、重大疾病体外诊断检测技术、新型药物系统体内治疗易复发难治愈疾病、神经免疫与再生五个方向；课题组承担多项国家级和省部级项目，在线粒体氧化磷酸化功能改变、新冠病毒快速检测试剂方面取得突破，发表高水平论文百余篇。
-- **卫生检验检疫**：负责人金大志研究员，研究新发突发传染病病原体检测检验新技术方法开发（艰难梭菌致病机制、耐药机制、基因组进化、小分子药物开发）及卫生检验技术；获省科技进步二等奖、三等奖各一项，省医药卫生科技进步一等奖一项、二等奖两项、三等奖一项，中科院一二区论文85篇，主编教材12部、主审7部。
-- **医学影像技术**：负责人徐秀芳教授，研究多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位；获国家自然科学基金3项、省部级项目20多项，全国优秀教材二等奖一项。
-- **康复治疗**：负责人倪湘明教授（附属人民医院），研究技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病；团队获国家级课题23项、省级课题23项，省科技进步三等奖2项、省医药卫生科技进步奖二等奖2项，国家发明专利和实用新型专利77项，SCI论文150篇，主编专业书籍、主审8部教材、参编书籍40多部。
-- **智能医学工程**：负责人李凯教授，研究脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病（阿尔茨海默病、帕金森病、抑郁症、自闭症）智能诊断及数字方向；主持参与国家级项目3项、省部级重点研发计划及200万以上重大设计项目，与中国人民解放军总院、浙一医院、日本文化研究所等单位开展合作；与浙大联合研制的阿尔茨海默病数字预警仪已申报二类医疗器械。
+- **医学检验技术**：负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制研究、新发突发传染病新型生物标志物筛选及致病机制研究、重大疾病体外诊断检测技术研究、新型药物系统体内治疗易复发难以治愈疾病研究、神经免疫与再生研究五个小方向；课题组承担多项国家级和省部级项目，在线粒体氧化磷酸化功能改变、线粒体相关疾病、新冠病毒快速检测试剂方面取得突破，发表高水平论文百余篇。
+- **卫生检验检疫**：负责人金大志研究员，研究内容为新发突发传染病病原体检测检验新技术方法开发（艰难梭菌致病机制、耐药机制、基因组进化、小分子药物开发）及卫生检验技术研究；获省科技进步二等奖、三等奖各一项，省医药卫生科技进步一等奖一项、二等奖两项、三等奖一项，中科院一二区论文85篇，主编专业教材12部、主审7部。
+- **医学影像技术**：负责人徐秀芳教授，研究内容为多参数MRI、肿瘤分子影像学、神经导航引导的脑肿瘤穿刺技术、脑肿瘤术前功能区定位四个方向；获国家自然科学基金3项、省部级项目20多项、全国优秀教材二等奖一项。
+- **康复治疗**：负责人倪湘明教授（附属人民医院），研究内容为技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病五大块；谢夏明教授团队获国家级课题23项、省级课题23项、省科技进步三等奖2项、省医药卫生科技进步奖二等奖2项、国家发明专利和实用新型专利77项、SCI论文150篇，主审教材8部、参编书籍40多部。
+- **智能医学工程**：负责人李海教授，研究内容为脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病智能诊断及数字方向五个方面；主持参与国家级项目3项、省部级重点研发计划及200万以上重大设计项目；与浙大联合研制的阿尔茨海默病数字预警仪已申报二类医疗器械。
 ## 师资队伍与领军人物
-- **师资总体**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，其中正高35人、博士46人；专业背景涵盖临床检验诊断学、医学检验技术、影像技术、康复治疗学、智能医学工程、生化分子、免疫生物技术、微生物学、细胞生物学。
-- **人才称号**：教育部医学技术类专业技能教授委员会委员、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。
-- **吕建新教授**：学位点负责人，国家百千万人才工程入选者、国家行业企业专家、15万人计划技术人才、领军人才，教育部医学技术类专业教学指导委员会委员、国家自然基金会医学技术检验学科专家组长、中华医学会检验学会教育学组组长；主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目、省科技重点研发应急公关项目等十余项，发表高水平论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项。
+- **队伍规模**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，其中正高35人、博士46人。
+- **人才称号**：教育部医学技术类专业技能教授委员会委员1人、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。
+- **吕建新教授**：学科领军人物、学位点负责人，国家百千万人才工程入选者、15万人计划技术人才、教育部医学技术类专业教学指导委员会委员、国家自然基金会医学技术检验学科专家组组长、中华医学会检验学会教育学组组长；主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表高水平论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项。
 - **徐秀芳教授**：浙江省151人才第3层次、省高校中青年学科带头人、研究生院院长、医学影像学院院长、国家一流本科专业建设点医学影像技术专业负责人、教育部教指委相关医学分会委员、中华医学会影像技术分会影像技术专委会委员；近三年以通讯作者或第一作者发表多篇高水平论文。
-- **叶祥明教授**：省人民医院主任医师、二级教授、博导、博士后导师，省康复中心主任、康复学院院长、省卫生领军人才、国家区域医疗中心浙江省重点培育专科康复医学学科带头人、数字化康复装备省部研究中心常务副主任；国家级课题3项、省重大课题2项，SCI论文98篇。
-- **金大志研究员**：博士、硕导，美国华盛顿大学博士后、美国MSCC访问学者，省创新人才、卫生创新人才、省首届优秀医疗机器人才，检验医学院学术院长、目标生物局体外诊断转化重点实验室主任、中国医师协会临床微生物分会常务委员；主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划、省自然基金重点项目、省部共建重大项目25项，SCI论文50多篇，参编专著6部，获省科技进步二等奖1项、三等奖1项及美国微生物学年会重要奖项、亚太临床微生物和感染年会travel奖。
-- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士、早稻田大学访问学者、师范大学特聘教授，智能医学前沿交叉学科研究院执行院长、智能医学学科负责人、浙江省中医药大学学科带头人；参与国家级项目，研制全生命周期中医治疗及康复医疗体系3套。
+- **叶祥明教授**：省人民医院主任医师、二级教授、博导、博士后导师，省康复学院院长、省卫生领军人才、国家区域医疗中心浙江省重点培育专科康复医学学科带头人、数字化康复装备省部研究中心常务副主任；获国家级课题3项、省重大课题2项，发表SCI论文98篇。
+- **金大志研究员**：博士、硕导，美国华盛顿大学博士后、美国MSCC访问学者，省创新人才、卫生创新人才、省首届优秀医疗机器人才，检验医学院学术院长、省生物标志物与器官诊断转化重点实验室主任、中国医师协会临床微生物分会常务委员；主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划、省自然基金重点项目及省部共建重大项目25项，发表SCI论文50多篇，参编专著6部，获省科技进步奖二等奖、三等奖各一项。
+- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士、早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长、智能医学学科负责人、浙江省中医药大学学科带头人、智慧健康装备国际平台主任；参与研制全生命周期中医治疗及康复医疗体系设备3台（套）。
 ## 硕士培养与毕业去向
-- **培养目标**：面向健康中国发展需要，服务区域行业产业发展，围绕国际学术前沿、国际重大需求和转化研究，培养熟练掌握医学技术领域专业知识技能、具有创新实践能力的高层次应用型人才。
-- **培养方式与学制**：教学专业实践与学位论文相结合；全日制专业学位学制三年，最长不超过五年。
-- **课程与学分**：课程包括公共学位课、专业学位课和专业选修课，实行学分制；毕业前学业课程不少于24学分，专业必修课分方向、学分大于等于12学分，专业选修课（智慧医疗、中医康复治疗学、生物信息学等）需达到5-6个学分以上。
-- **培养环节**：第二学期准备开题，第三、第四学期（研二）过程性考核结束，研一第二学期进行学位论文答辩。
-- **医院就业**：检验方向可进入检验科、输血科、病理科；影像技术方向可进入放射科、超声科；康复治疗方向可进入康复医学科、骨科、神经科、运动医学科等。
-- **疾控与公共卫生**：卫检方向可进入疾病预防控制中心（CDC），参与传染病防控、慢性病防治等公共卫生工作。
-- **企业就业**：医药企业与生物技术公司（研发、生产、市场销售、质量管理法规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）。
-- **公务员与事业单位**：可进入药监局、卫健委、海关，从事医疗器械监管、卫生政策制定、口岸卫生检疫等工作。
-- **继续深造**：可到高校、研究所读博或从事研究工作；举例东阳市卫健委疾控中心招聘检验方向微生物检验岗位要求硕士及以上。
+- **培养目标**：面向健康中国发展需要，服务区域行业产业发展，围绕国际学术前沿、国际重大需求和转化研究，培养熟练掌握医学技术领域专业知识技能、具有良好创新实践能力的高层次应用型人才。
+- **培养方式**：采用教学、专业实践与学位论文相结合的方式；全日制专业学位学制三年，最长不超过五年。
+- **学分要求**：实行学分制，毕业前学业课程不少于24学分，其中专业必修课分方向≥12学分，专业选修课（智慧医疗、中医康复治疗学、生物信息学等）需达5-6学分。
+- **培养环节**：第二学期准备开题，第三、第四学期（研二）完成过程性考核，研一第二学期进行论文答辩。
+- **医院就业**：检验方向可进入检验科、输血科、病理科；影像技术方向可进入放射科、超声科；康复治疗方向可进入康复医学科、骨科、神经科、运动医学科等科室。
+- **疾控与公卫**：卫检方向可进入疾病预防控制中心（CDC），参与传染病防控、慢性病防治等公共卫生工作。
+- **企业就业**：医药企业与生物技术公司（研发、生产、市场销售、质量管理与法规合规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）。
+- **公务员与深造**：可进入药监局、卫健委、海关从事医疗器械监管、卫生政策制定及口岸卫生检疫；也可到高校、研究所继续读博或从事研究工作。
 ## 2026年招考计划
 - **招生计划**：2026年计划招生34人，仅供参考，以教育部正式下达人数为准。
-- **初试科目**：思想政治理论、英语为统考，专业课为自主命题，按方向设检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合；检验技术专业课考分子生物学检验、生物化学检验、微生物学检验。
-- **考试大纲**：专业综合课程为指定性考试大纲，实践分值300分、考试时长180分钟；检验综合中卫生生物学检验占40%、生物化学检验占30%、微生物学检验占30%；大纲含考试内容、形式、试卷结构、知识点及参考书目，以杭州医学院研究生招生网公布为准。
-- **复试方式**：线上线下结合，目前以线下为主；初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%；导师采取双选制。
+- **初试科目**：思想政治理论、英语为统考科目；专业课为自主命题，按方向考检验综合、医学影像技术综合、康复治疗综合或智能医学工程综合。
+- **检验综合内容**：考分子生物学检验、生物化学检验、微生物学检验，占比分别为40%、30%、30%。
+- **考试大纲**：专业综合课程为指定性考试大纲，包括考试内容、形式、试卷结构、知识点及参考书目；实践分值300分，考试时长180分钟。
+- **信息渠道**：杭州医学院研究生招生网（myz.emc.edu.cn）及研究生教育微信公众号公布考试方向、大纲及参考教材。
+- **复试方式**：采用线上线下结合，目前以线下为主；初试占60%、复试占40%。
+- **复试内容**：英语能力测试占20%、专业能力测试占40%、综合能力测试占40%；导师采取双选制。
 # 各方立场与诉求
-- **主持人**：代表后台考生提问，关注当前经济形势下医学技术专业研究生毕业后的就业前景，并询问暑期备考初试科目。
-- **宋宝峰**：回应就业前景问题，强调国家就业优先政策，指出毕业生可继续深造读博，或进入三甲医院、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等单位，就业面宽广且有竞争力；杭州高水平三甲医院和企业对研究生及以上学位具有核心竞争力，考生不必过度担心和焦虑。
-- **主持人**：追问硕士研究生入学考试初试科目有哪些，以便考生利用暑期时间准备。
-- **宋宝峰**：回应初试科目共三门，思想政治理论和英语为统考，专业课为自主命题，按报考方向分别考检验综合、医学影像技术综合、康复治疗综合或智能医学工程综合；英语难度介于四级和六级之间，暑期是关键备考时期，建议关注杭州医学院研究生招生网和研究生教育微信公众号获取考试大纲与参考教材。
-- **主持人**：代考生询问跨专业报考问题，考生担心非本专业背景节奏跟不上。
-- **宋宝峰**：明确回应允许非本专业考生跨专业报考医学技术专业，如检验方向可跨专业自主报考，鼓励跨学科跨专业报考，并指出跨专业报考被录取的概率会大大提高。
-- **主持人**：提及后台考生关于交通和竞赛的问题，询问学校地理位置及研究生能否参加学科竞赛。
-- **宋宝峰**：回应学校有三个校区，主城区黄路校区交通便利；学校重视竞赛，有资源提升改善、专门讲座和培训，研究生在竞赛中取得好成绩，以赛促学、以赛促教、以赛促改。
+- **主持人**：代表后台考生提出就业前景关切，询问在当前经济形势下医学技术专业研究生毕业后的就业出路。
+- **宋宝峰**：回应称就业前景非常好，毕业生可继续深造读博，也可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校及研究所等单位；强调杭州有大量高水平三甲医院和企业，研究生及以上学位具有核心竞争力，考生不必过度担心和焦虑。
+- **主持人**：代考生询问暑期备考初试科目应如何准备。
+- **宋宝峰**：回应称初试共三门，思想政治理论和英语为统考，专业课按方向自主命题；英语难度介于四级和六级之间，暑期是关键备考期，建议英语达到四级水平并参考研究生考试英语真题，专业课聚焦学校研究生招生网公布的考试大纲与参考教材。
+- **主持人**：代考生询问非本专业考生能否跨专业报考医学技术专业。
+- **宋宝峰**：明确表示允许跨专业报考，鼓励非本专业考生报考，如检验方向可接受跨专业考生；主持人补充称跨专业报考被录取概率会大大提高，宋宝峰予以确认。
+- **主持人**：提及后台考生关注交通与竞赛问题。
+- **宋宝峰**：回应称学校有三个校区，主校区位于主城区、交通便利；学校重视竞赛，有资源提升改善、专门讲座与培训，研究生在竞赛中取得好成绩，以赛促学、以赛促教、以赛促改。
 # 达成共识
-- **学位点定位**：医学技术专业硕士点为2024年获批的新学位点，由检验学院、生物工程学院（合署办公）牵头，医学影像学院、康复学院、信息工程学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向。
-- **招生口径**：2026年计划招生34人，宋宝峰明确**该人数仅供参考，实际招生以教育部正式下达人数为准**，并强调2025年实际录取64人。
-- **初试科目**：确认初试共三门，思想政治理论、英语为统考，专业课按方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）。
-- **复试口径**：确认复试以线下为主，初试占60%、复试占40%，复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%，导师采取双选制。
-- **跨专业报考**：宋宝峰明确**允许非本专业考生跨专业报考医学技术专业**，如检验方向可跨专业报考，并确认跨专业报考被录取概率会大大提高。
-- **就业前景**：确认就业面广，可进入医院相关科室、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校及研究所，并可继续读博深造；杭州高水平三甲医院和企业对研究生及以上学位有核心竞争力。
-- **备考指引**：确认英语考试难度介于四级和六级之间，暑期为备考关键时期，建议关注杭州医学院研究生招生网和研究生教育微信公众号获取考试大纲、参考书目等信息。
+- **学位点定位**：医学技术专业硕士点为2024年获批的新学位点，由检验医学院、生物工程学院（合署办公）牵头，联合医学影像学院、康复学院、信息工程学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向。
+- **招生口径**：2025年已录取64名考生（检验方向38人、经济方向11人、康复方向13人、职业方向24人）；2026年计划招生34人，**仅供考生参考，实际招生人数以教育部2026年正式下达人数为准**。
+- **初试科目口径**：初试共三门，思想政治理论、英语为统考科目，专业课为学校自主命题，按报考方向分别考检验综合、医学影像技术综合、康复治疗综合或智能医学工程综合；检验技术专业课考分子生物学检验、生物化学检验、微生物学检验。
+- **复试口径**：复试目前以线下为主，初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%，导师采取双选制。
+- **跨专业报考口径**：**允许非本专业考生跨专业报考医学技术专业**（如检验方向可跨专业自主报考），宋宝峰明确表示「可以跨专业自主报考的啊，这个大家放心」，并指出跨专业报考被录取概率会大大提高。
+- **就业前景口径**：就业面覆盖医院相关科室、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校及研究所等，也可继续读博深造；杭州有高水平三甲医院和企业，研究生及以上学位具有核心竞争力。
+- **备考口径**：英语考试难度介于四级和六级之间，暑期是关键备考时期；考生可通过杭州医学院研究生招生网（myz.emc.edu.cn）及研究生教育微信公众号获取考试大纲、参考教材等详细信息。
 # 待协调事项与后续
 ## 待协调事项
-- **2026年计划招生人数**：初试计划招生34人，仅供考生参考，实际招生人数以教育部2026年正式下达人数为准
-- **复试具体形式与内容**：以学校届时公布的复试录取办法为基础，目前可参考2025年复试办法
+- **2026年实际招生人数**：以教育部正式下达人数为准，当前计划招生34人仅为参考
+- **复试具体形式与内容**：以学校复试录取办法为基础，目前可参考2025年复试办法
 ## 后续安排与参与方式
-- **官方信息渠道**：杭州医学院研究生招生网（myz.emc.edu.cn），考生需经常关注招生动态
-- **微信公众号**：关注「杭州医学院研究生教育」微信公众号，可查看考试方向、大纲及参考教材书籍
-- **初试科目**：思想政治理论、英语为统考科目；专业课按方向自主命题，分别为检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合
-- **专业课考试内容**：检验技术考分子生物学检验、生物化学检验、微生物学检验；检验综合中卫生生物学检验占40%、生物化学检验占30%、微生物学检验占30%
-- **考试大纲**：专业综合课程为指定性考试大纲，含考试内容、形式、试卷结构、知识点及参考书目；实践分值300分，考试时长180分钟
-- **复试安排**：目前以线下为主，初试占60%、复试占40%；复试含英语能力测试20%、专业能力测试40%、综合能力测试40%，导师采取双选制
-- **备考建议**：暑期为备考关键时期；英语难度介于四级和六级之间，可参考研究生考试英语真题；思政需与时俱进学习
-- **跨专业报考**：允许非本专业考生跨专业报考医学技术专业（如检验方向），跨专业报考被录取概率会大大提高
-- **直播回看**：本场直播结束后24小时内上传至B站，考生可随时搜索回看
-- **学校校区**：学校有滨江校区、黄路校区（主城区）等三个校区，主城区校区交通便利</t>
+- **直播回看**：本场直播结束后24小时内上传至B站，可随时搜索回看
+- **研究生招生网**：myz.emc.edu.cn（杭州医学院研究生招生网），可查询考试大纲、参考书目、招生方向等详细信息
+- **微信公众号**：关注「杭州医学院研究生教育」公众号，获取考试方向、大纲、参考教材与书籍等信息
+- **学校官网**：持续关注杭州医学院官网获取更多报考信息
+- **备考建议**：暑期为关键备考时期，英语难度介于四级和六级之间，建议达到四级水平并参考研究生考试英语真题
+- **跨专业报考**：允许非本专业考生跨专业报考医学技术专业（如检验方向），跨专业报考被录取概率会大大提高</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>102.2</v>
+        <v>99.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23026/6252</t>
+          <t>23026/5747</t>
         </is>
       </c>
     </row>
@@ -11840,71 +11738,72 @@
       <c r="C32" t="inlineStr">
         <is>
           <t># 课程概况
-本次课程为历史小论文写作方法指导课，由主讲人面向学生讲解小论文写作要求与解题技巧。课程围绕三大核心内容展开：**小论文写作的基本要求**（观点明确、论证条理、结论升华）、**按题型分类的解题方法**（自命题类、观点提示类、图表信息类），以及**典型例题的实操分析**（武汉长江大桥、梁启超观点、历代民德等级变化等）。课程通过学生现场呈现思路、主讲人逐一点评的方式，结合官方答案示例，帮助学生掌握审题、读材料、列事实、控制篇幅等关键步骤。
+本次课程为历史小论文写作专题指导课，由老师主讲，围绕小论文写作的核心方法展开，重点讲解观点提炼、论证结构、审题步骤及自命题类、观点提示类、图表信息类等题型的解题技巧。老师强调小论文写作须先亮明观点，观点要明确、有凝聚力，论证部分一般写两到三条，内容先写背景学术报告再结合自身观点，论述逻辑需清晰，可按时间脉络或国内外分类，结尾须升华观点而非简单重复。课程通过武汉长江大桥、1940年抗战时期材料评析等例题进行实践分析，指导学生结合历史背景与中华文化优越性（如丝绸之路、四大发明）展开论证，并强调审题时注意材料关键信息与“小红帽”要求，写作须体现重大国家利益。
 # 核心知识点梳理
-## 小论文写作总体要求
-- **观点明确**：必须亮出自己的观点，不能只是简单陈述形式或写几个方面加名词；观点要有凝聚力，如「辉煌的中华文化」这类表述需进一步明确立场。
-- **论证条数**：论证一般写**两到三条**，不宜过多；写一条难以支撑论点，写太多则显得冗长。
-- **逻辑清晰**：可通过序号或直接列条呈现，但必须让老师看清写了哪几条；可按**时间脉络**（如先秦、明清时期）、**国内外**、**内因外因**等维度组织。
-- **结论升华**：最后论述要**简便**，目的是升华观点，不能简单把观点抄一遍；结论需体现对观点的深化而非重复。
-## 自命题类解题方法
-- **审题**：先慢审题，看要求，注意「小红帽」要求及评分标准；如题目要求用世界史知识，不能写成中国史模式。
-- **读材料**：先大概看材料抓主要信息，再细看信息之间的关系；提取有效信息后再进行分析。
-- **列事实**：先写好题目，再罗列与材料相关的事实，不能乱罗列；事实需与材料有关系。
-- **控制篇幅**：最好先打草稿，不要直接写在答题卡上，避免写错后涂改混乱。
-- **案例：武汉长江大桥**：可写新中国成立或改革开放以来的背景；按时间顺序应**先写对内改革，再写对外开放**；需明确具体时间节点，不能笼统说「新中国成立后」。
+## 小论文写作基本要求
+- **观点明确**：写作必须先亮明观点，观点要**有凝聚力**，不能只是简单陈述几个方面加个名词，也不是简单陈述一个形式。
+- **论证条数**：论证一般写**两到三条**，不宜过多；写一条难以支撑论点，太多则显得冗长。
+- **内容结构**：先写背景学术报告，再结合自己的观点；论述逻辑要清晰，可按时间脉络（如先秦、明清时期）或国内外、内政外交等分类罗列。
+- **结尾升华**：最后论述要**升华观点**，不能简单把观点抄一遍；写结尾是为了升华观点，需简明扼要。
+## 自命题类解题步骤
+- **审题**：先阅读题目、**慢点审题**，注意要求中的“小红帽”及形成标准；如要求用世界史知识就不能用中国史内容。
+- **读材料**：认真读材料，先大概看抓主要信息，再细看材料之间的关系；提取有效信息后再进行分析。
+- **列事实**：先写好题目，再罗列要写的事实，事实要与材料相关，不能乱罗列；建议先在草稿上写好再誊写。
+- **论述**：最后进行论述，注意升华观点；写作要体现**重大国家利益**，如武汉长江大桥例题需结合新中国成立、改革开放等背景。
 ## 观点提示类解题方法
-- **选择核心观点**：需判断并选择一个核心观点，明确表述「我认为什么观点是正确的或错误的」；不同观点要在论点中详细表述。
-- **不能照抄材料**：写小论文时不能照抄材料观点，需用自己的语言表述。
-- **总结升华**：最后需简单总结观点并进行升华。
-- **案例：梁启超观点**：材料含四个观点，如「国民对其本国历史应略有所知」「了解本国历史会对我国利益有威胁」「对本国历史有敬畏不会偏激理解」「国家才能继续发展」；需选一个观点展开论证，不能重复材料观点。
-- **案例：历代民德等级变化**：可写春秋、东汉、宋明等时期；需结合时代背景分析，如唐朝国力强盛但民德较高，与制度改善有关；可联系儒家思想等文化因素。
+- **选观点**：先看材料中有哪些观点，选择一个**核心观点**；必须明确自己的判断，如“我认为某观点是正确的/错误的”。
+- **不照抄**：不能照抄材料观点，要形成自己的观点；写论文题目时不能只写一句诗作为观点，必须表明自己的看法。
+- **论证角度**：可结合历史背景与中华文化优越性论证，如丝绸之路、四大发明对欧洲的贡献；注意材料写作的时代背景（如1940年抗战时期）。
+- **总结升华**：最后要简单总结观点并进行升华；观点提示类与评析材料观点的区别在于要**提出自己的看法**，而非直接评析材料观点。
 ## 图表信息类解题方法
-- **快速提取信息**：先看图表题头、横向纵向信息，注意信息之间的关系变化；提取有效信息后再进行分析。
-- **案例：建筑与政治关系**：材料展现两三个图线，涉及建筑与政治的关系；需从建筑角度分析其与政治的联系。
-- **案例：历史地图题**：需在地图上画位置，结合地图信息作答；如涉及707年、1900年等时间点。
-- **案例：欧盟框架图**：涉及共同体、共同外交安全政策、司法和内部合作等大框架；需提取三个信息并分析其关系，再下结论。
-- **难点标注** ⭐：图表信息类题目较难，需注意信息间的关系变化，不能只看表面数据。
+- **看关键信息**：快速看图表关键信息，包括题头、横向纵向信息；注意信息之间的关系变化。
+- **提取分析**：提取有效信息后再进行分析；如历史地图题需在地图上画位置，注意时间信息（如707年、1900年）。
+- **关系判断**：注意图表中信息之间的关系，如共同体、共同外交安全政策、司法和内部合作的大框架制度内的小信息关系；提取三个信息后判断关系并下结论。
+- **例题应用**：如建筑类图表题展现两三个图线，需从建筑与政治的关系角度分析；图表信息类题目需快速提取关键信息，分析关系变化。
 # 课堂互动与答疑
-**学生**：小论文论证部分写几条比较合适？写一条或太多条会有什么问题？
-**教师**：论证一般写两到三条，不宜过多。写一条难以支撑论点，写太多则显得冗长且逻辑易散。关键是每条论证都要能有效支撑你的观点，逻辑清晰，让老师能清楚看到你论述的层次。
-**学生**：自命题类题目，审题时除了看要求，还有什么特别要注意的？
-**教师**：审题时要注意题目要求里的"小红帽"——即那些关键限定条件，比如要求用世界史知识还是中国史知识，或限定在某个范围。这些限定直接影响你选材和论述方向，漏看会导致整篇跑题。
-**学生**：写小论文时，事实罗列有什么讲究？可以直接写在答题卡上吗？
-**教师**：不要直接写在答题卡上。先在草稿上写好题目，再罗列要用的史实，确保这些事实与材料相关、能支撑论点，避免乱罗列。理清顺序后再誊写，防止写错或逻辑混乱。
-**学生**：观点提示类题目，能不能直接照抄材料中的观点？
-**教师**：不能照抄。你需要从材料给出的多个观点中选择一个核心观点，用自己的语言明确表述，并表明你赞同或反对的态度。照抄材料观点无法体现你的独立判断，也难形成自己的论述立场。
-**学生**：图表信息类题目，如何快速从图表中提取有效信息？
-**教师**：先看题头和横向、纵向栏目，把握图表的基本框架；再观察各项信息之间的变化趋势和相互关系，比如时间序列上的升降、不同类别的对比。提取有效信息后再结合所学知识进行分析，不要只停留在描述图表表面数据。
-**学生**：写结论时，直接重复开头观点可以吗？
-**教师**：不可以。结论的作用是升华观点，不能简单把开头观点抄一遍。要在论证基础上提炼出更深层的认识或启示，使文章立意提升，这才是有价值的收尾。
+**学生**：小论文论证部分一般写几条比较合适？写一条或太多条会有什么问题？
+**教师**：论证一般写两到三条。写一条往往无法充分支撑论点，写太多条则容易导致每一条都论证不充分、内容单薄。关键是每条论证都要能真正支撑你的观点，宁少勿滥。
+**学生**：论述部分的逻辑怎么安排才能让老师看清楚？
+**教师**：论述逻辑必须清晰，可以按时间脉络（如先秦、宋明、明清时期）、空间维度（国内/国外）或内外因素等分类展开。无论用哪种方式，都要让阅卷老师一眼看清你写了哪几条、分别对应什么层次，不能含糊堆叠。
+**学生**：最后的总结论述应该怎么写？
+**教师**：总结论述是为了升华观点，不能简单把开头观点再抄一遍。要结合前文论证，提炼出更深层的认识或意义，让结尾有提升感。
+**学生**：自命题类题目第一步应该注意什么？
+**教师**：先审题，要慢审，看清题目要求，特别注意要求中的“小红帽”和形成标准。比如题目要求用世界史知识，就不能写成中国史；题目限定了范围，就不能超出。审题不清是这类题失分的主要原因。
+**学生**：读材料时应该怎么抓重点？
+**教师**：先大概浏览材料，抓主要信息，再细看各部分之间的关系。提取事实时要跟材料有关联，不能乱罗列。罗列事实前先想好要写哪几条，再动笔写题目，最后才正式作答，避免写错涂改。
+**学生**：观点提示类题目和自命题类有什么区别？
+**教师**：观点提示类题目会先给出若干观点，你要从中选择或判断一个核心观点，明确表态“我认为某观点正确/错误”，不能照抄材料观点。自命题类则要自己提炼观点。观点提示类还要注意不能重复材料中的观点表述。
+**学生**：图表信息类题目怎么快速提取信息？
+**教师**：先看图表的关键信息，包括题头、横向纵向栏目分别代表什么，再注意这些信息之间的关系和变化趋势，提取有效信息后结合材料进行分析。图表类题目往往信息量大，要抓住主要变化和关键节点。
+**学生**：评析材料观点时，为什么还要关注材料写作的时代背景？
+**教师**：材料写于什么年代直接影响作者意图和观点倾向。比如1940年抗战时期写的材料，其观点必然带有应对抗战现实的目的。不结合时代背景，就无法准确理解作者为什么这样写、为什么强调这些内容，论证就会缺乏深度。
 # 课后任务与学习建议
 ## 课堂练习
-- **自命题类（武汉长江大桥）**：先审题看要求（注意小红帽要求与形成标准），再读材料抓主要信息、细看关系；先写题目再罗列与材料相关的事实，控制篇幅。可写新中国成立或改革开放以来，按时间顺序先对内改革后对外开放。
-- **观点提示类（梁启超观点）**：材料给出四个观点，需选择其中一个核心观点明确表述，不能照抄材料观点；论证时结合史实支撑（如中华文化优越性、四大发明对欧洲贡献），最后总结升华。学生选第二条（对本国历史应有敬畏）获主讲人认可。
-- **观点提示类（历代民德等级变化）**：结合图表中历代民德等级变化，可写春秋、东汉、宋明等时期；联系儒家思想、社会状态分析原因，如唐朝国力强盛但民德较高，需推论国家强盛、民德高尚与制度改善的关系。
-- **图表信息类（建筑与政治关系）**：快速查看图表题头、横向纵向信息，注意信息间关系变化；提取有效信息（如建筑风格与政治制度对应）进行分析，再结合材料与实践关系进行论述。
+- **武汉长江大桥例题**：自命题类练习，考点为新中国成立与改革开放背景下的重大国家利益。要点是审题看清要求，结合材料关键信息，按时间顺序先写对内改革再写对外开放，论述需体现国家利益。
+- **1940年抗战时期材料评析**：观点提示类练习，材料含四个观点，学生选第二个（国民应了解本国历史）。论证需结合中华文化优越性，如丝绸之路、四大发明对欧洲贡献，并说明1940年抗战时期写作背景。
+- **历代民德等级图表题**：图表信息类练习，考点为图表关键信息提取与关系分析。需看题头、横向纵向信息，分析民德等级变化与时代关系，可结合儒家思想、社会状态等因素论证。
+- **建筑与政治关系题**：图表信息类练习，通过建筑图片分析建筑与政治的关系，提取有效信息后结合材料与实践关系进行论述。
 ## 复习重点
-- **小论文写作要求**：观点必须明确亮出，不能只是简单陈述形式或几个方面加个名词；论证一般写两到三条，不宜过多也不宜太少，需支撑论点、逻辑清晰。
-- **论证组织方式**：可用序号或直接列出，但逻辑要非常清晰，让老师看清写了几条；可按时间脉络（如先秦、明清时期）、国内外、内政外交等角度罗列，但必须清楚呈现。
-- **结论升华要求**：最后论述要简便并升华观点，不能简单把观点抄一遍；写结论是为了升华观点，需注意与前面论证的呼应。
-- **自命题类解题步骤**：先审题看要求（注意小红帽要求与形成标准），再读材料抓主要信息、细看关系，先写题目再罗列与材料相关的事实，最后进行论述。
-- **观点提示类解题要点**：需选择核心观点并明确表述，判断观点正确或错误；不能照抄材料观点，需用自己的理解表述，最后总结升华。
-- **图表信息类解题方法**：快速查看图表关键信息（题头、横向纵向信息），注意信息间关系变化，提取有效信息进行分析。
+- **观点明确**：小论文必须亮明观点，观点要有凝聚力，不能只是简单陈述几个方面加名词，要形成自己的判断。
+- **论证结构**：论证一般写两到三条，不宜过多，要能支撑论点；内容先写背景学术报告，再加自己的观点。
+- **论述逻辑**：逻辑要清晰，可按时间脉络（如先秦、明清时期）或国内外、内外因分类罗列，让老师清楚看到写作层次。
+- **结尾升华**：最后论述要升华观点，不能简单重复观点，要提炼出更深层的意义。
+- **审题要点**：注意题目要求中的"小红帽"和形成标准，看清是否限定世界史知识或特定范围。
+- **观点提示类方法**：先看有哪些观点，选择核心观点，明确自己的判断（正确或错误），不能照抄材料，最后总结观点并升华。
 ## 学习建议
-- **审题要慢**：主讲人强调"你要慢点审题"，看要求里是否有小红帽要求及形成标准，注意题目限定范围（如用世界史知识、限定在某人某事范围内）。
-- **先写题目再列事实**：不要直接写在答题卡上，先写好题目，再罗列要写的事实，确保事实与材料相关，避免写错又乱。
-- **论证条数控制**：论证部分写两到三条即可，写一条难以支撑论点，写太多则显得冗长；每条论证需与材料相关，不能乱罗列。
-- **结合时代背景分析**：写观点提示类题目时，需思考作者为何在特定时期写此内容（如1940年抗战时期钱穆写《国史大纲》），结合时代背景分析写作目的。
-- **注意时间顺序**：写背景时按时间顺序排列，如先写对内改革再写对外开放，不要颠倒顺序。</t>
+- **先写草稿再誊写**：不要直接写在答题卡上，先在草稿纸上写好题目，罗列事实，避免写错又乱。
+- **罗列事实要相关**：罗列的事实要与材料有关系，不能乱罗列，先想好再写。
+- **审题要慢**：审题要慢，看清要求，注意"小红帽"要求及形成标准，再读材料抓主要信息。
+- **图表题快速提取**：看图表先抓题头、横向纵向信息，注意信息之间的关系变化，再提取有效信息分析。
+- **结合时代背景**：写历史小论文要结合时代背景，如1940年抗战时期文人的写作目的，不能脱离历史语境。</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>41.7</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12357/3330</t>
+          <t>12357/3246</t>
         </is>
       </c>
     </row>
@@ -12061,118 +11960,103 @@
       <c r="C33" t="inlineStr">
         <is>
           <t># 报告概况
-十四届全国人大三次会议于2025年开幕，出席代表2880人，符合法定人数，会议第一项议程为审议政府工作报告。国务院总理李强代表国务院作报告，回顾2024年工作，提出2025年经济社会发展主要预期目标及政府工作任务。报告指出，2024年国内生产总值达**134.9万亿元**、增长**5%**，城镇新增就业1256万人，粮食产量首次跃上1.4万亿斤新台阶，全年经济社会发展主要目标任务顺利完成；2025年经济增长预期目标为**5%左右**，赤字率拟按**4%左右**安排，合计新增政府债务总规模11.86万亿元，并部署大力提振消费、发展新质生产力、保障改善民生等十大方面任务。报告整体基调为迎难而上、奋发有为，强调坚持稳中求进工作总基调，高质量完成“十四五”规划目标任务。
+十四届全国人大三次会议于2025年3月5日开幕，出席代表2880人、缺席49人，出席人数符合法定人数，会议第一项议程为审议政府工作报告，由国务院总理李强代表国务院作报告。报告回顾2024年工作，提出2025年经济社会发展总体要求、主要预期目标和政府工作任务，整体基调为坚定信心、迎难而上，确保“十四五”规划圆满收官。2024年国内生产总值达**134.9万亿元**、增长**5%**，城镇新增就业1256万人，粮食产量首次跃上1.4万亿斤新台阶，全年经济社会发展主要目标任务顺利完成；2025年主要预期目标为国内生产总值增长**5%左右**、城镇新增就业1200万人以上、居民消费价格涨幅2%左右，宏观政策取向为实施更加积极的财政政策和适度宽松的货币政策，赤字率拟按4%左右安排、赤字规模5.66万亿元，合计新增政府债务总规模11.86万亿元。报告部署2025年政府工作任务十个方面，涵盖扩大内需、发展新质生产力、科教兴国、改革开放、防范化解风险、乡村振兴、绿色转型、民生保障等领域，并明确今年将开展“十五五”规划编制工作。
 # 核心政策
-- **2025年经济社会发展主要预期目标**：国内生产总值增长**5%左右**；城镇调查失业率**5.5%左右**；城镇新增就业**1200万人以上**；居民消费价格涨幅**2%左右**；居民收入增长和经济增长同步；国际收支保持基本平衡；粮食产量**1.4万亿斤左右**；单位国内生产总值能耗降低**3%左右**；生态环境质量持续改善。
-- **财政政策**：今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；拟发行超长期特别国债**1.3万亿元**；拟发行特别国债**5000亿元**支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**。
-- **货币政策**：实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配；优化和创新结构性货币政策工具，促进楼市股市健康发展；推动社会综合融资成本下降。
-- **宏观政策民生导向**：经济政策的着力点更多转向惠民生、促消费，推动更多资金资源“投资于人”、服务于民生；健全和用好宏观政策取向一致性评估工作机制，提升政策目标、工具、时机、力度、节奏的匹配度。
-- **大力提振消费**：实施`提振消费专项行动`，制定提升消费能力、增加优质供给、改善消费环境专项措施；安排超长期特别国债**3000亿元**支持消费品以旧换新；扩大健康、养老、托幼、家政等多元化服务供给；加快数字、绿色、智能等新型消费发展。
-- **扩大有效投资**：今年中央预算内投资已安排**7350亿元**；用好超长期特别国债更大力度支持`两重建设`；优化地方政府专项债券管理机制；支持和鼓励民间投资发展。
-- **发展新质生产力**：深入推进战略性新兴产业融合集群发展，开展`新技术、新产品、新场景大规模应用示范行动`；培育生物制造、量子科技、具身智能、6G等未来产业；深入实施`制造业重大技术改造升级和大规模设备更新工程`；持续推进`人工智能+行动`，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端。
-- **科教兴国战略**：制定实施`教育强国建设三年行动计划`；加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育；加快组织实施和超前布局重大科技项目；从制度上保障企业参与国家科技创新决策、承担重大科技项目；大力支持和大胆使用青年科技人才。
-- **标志性改革举措**：高质量完成`国有企业改革深化提升行动`；加力推进清理拖欠企业账款工作，开展`规范涉企执法专项行动`；纵深推进全国统一大市场建设，综合整治`内卷式竞争`；修订出台新版市场准入负面清单；开展中央部门`零基预算改革试点`；深化资本市场投融资综合改革，大力推动中长期资金入市。
-- **高水平对外开放**：扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设；扩大电信、医疗、教育等领域开放试点；推动`高质量共建一带一路`走深走实；持续扩大面向全球的高标准自由贸易区网络。
-- **防范化解重点领域风险**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，推进收购存量商品房，有效防范房企债务违约风险；完善和落实一揽子化债方案，动态调整债务高风险地区名单，坚决遏制违规举债行为；一体推进地方中小金融机构风险处置和转型发展。
-- **乡村全面振兴**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`；确保不发生规模性返贫致贫；有序推进第二轮土地承包到期后再延长**30年**试点，扩大整省试点范围。
-- **新型城镇化与区域协调**：深入实施`新型城镇化战略行动`，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务；持续推进城市更新和城镇老旧小区改造；支持经济大省挑大梁，深化东中西东北地区产业协作。
-- **绿色低碳转型**：持续深入推进蓝天碧水净土保卫战；深入实施`绿色低碳先进技术示范工程`；积极稳妥推进碳达峰碳中和，建立一批零碳园区、零碳工厂，建立产品碳足迹管理体系、碳标识认证制度；加快建设沙戈荒新能源基地。
-- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业`就业支持计划`；支持劳动密集型产业吸纳和稳定就业；拓宽高校毕业生等青年就业创业渠道；加强灵活就业和新就业形态劳动者权益保障；开展大规模职业技能提升培训行动。
-- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革；实施`医疗卫生强基工程`；优化药品集采政策，健全药品价格形成机制，支持创新药发展；严格医保基金监管。
-- **社会保障和服务**：城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金；推进社区支持的居家养老，强化失能老年人照护；制定促进生育政策，发放育儿补贴，大力发展托幼一体服务。
-- **维护国家安全和社会稳定**：深入实施`安全生产治本攻坚三年行动`；抓好校园学生餐、平台外卖安全监管；推进基层综治中心规范化建设；建设更高水平的平安中国。
-- **十五五规划编制**：今年将开展`十五五规划编制工作`，科学确定发展目标，谋划好重大战略任务、重大政策举措、重大工程项目。
+- **2025年发展主要预期目标**：国内生产总值增长**5%左右**，城镇调查失业率**5.5%左右**，城镇新增就业**1200万人以上**，居民消费价格涨幅**2%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡，粮食产量**1.4万亿斤左右**，单位国内生产总值能耗降低**3%左右**，生态环境质量持续改善。
+- **财政政策**：实施更加积极的财政政策，今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；拟发行超长期特别国债**1.3万亿元**，拟发行特别国债**5000亿元**支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**，今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**。
+- **货币政策**：实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配；优化和创新结构性货币政策工具，更大力度促进楼市股市健康发展，推动社会综合融资成本下降。
+- **宏观政策民生导向**：经济政策的着力点更多转向惠民生、促消费，推动更多资金资源投资于人、服务于民生；健全和用好宏观政策取向一致性评估工作机制，提升政策目标、工具、时机、力度、节奏的匹配度。
+**扩大内需与产业发展**
+- **提振消费专项行动**：安排超长期特别国债**3000亿元**支持消费品以旧换新；制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力；扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展。
+- **扩大有效投资**：今年中央预算内投资已安排**7350亿元**；用好超长期特别国债更大力度支持`两重建设`，优化地方政府专项债券管理机制，支持和鼓励民间投资发展，坚决防止低效无效投资。
+- **发展新质生产力**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动；培育生物制造、量子科技、具身智能、6G等未来产业；深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型。
+- **数字经济创新**：持续推进`人工智能+`行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端；扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用。
+**科教兴国与改革开放**
+- **高质量教育体系**：制定实施`教育强国建设三年行动计划`，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育；扎实推进优质本科扩容，加快`双一流`建设。
+- **科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革；加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目；大力支持和大胆使用青年科技人才。
+- **标志性改革举措**：高质量完成国有企业改革深化提升行动，扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展`规范涉企执法专项行动`；纵深推进全国统一大市场建设，综合整治`内卷式竞争`，修订出台新版市场准入负面清单。
+- **财税金融改革**：开展中央部门`零基预算改革试点`，支持地方深化零基预算改革；加快推进部分品目消费税征收环节后移并下划地方；深化资本市场投融资综合改革，大力推动中长期资金入市。
+- **高水平对外开放**：扩大电信、医疗、教育等领域开放试点，推动自贸试验区提质增效和扩大改革任务授权；扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设；推动高质量共建`一带一路`走深走实。
+**风险防范与民生保障**
+- **房地产风险化解**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险；加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子。
+- **地方政府债务化解**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，坚决遏制违规举债行为。
+- **金融风险防范**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险；健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案。
+- **乡村全面振兴**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`；有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围；确保不发生规模性返贫致贫。
+- **新型城镇化**：深入实施新型城镇化战略行动，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务；强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系；持续推进城市更新和城镇老旧小区改造。
+- **绿色低碳转型**：协同推进降碳、减污、扩绿、增长，持续深入推进蓝天碧水净土保卫战；建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系和碳标识认证制度；加快建设沙戈荒新能源基地，开展煤电低碳化改造试点示范。
+- **就业优先**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业；拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障，开展大规模职业技能提升培训行动。
+- **医疗卫生服务**：深化以公益性为导向的公立医院改革，实施`医疗卫生强基工程`，优化药品集采政策，健全药品价格形成机制，支持创新药发展；严格医保基金监管，让每一分钱都用于增进人民健康福祉。
+- **社会保障**：城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金；推进社区支持的居家养老，强化失能老年人照护；制定促进生育政策，发放育儿补贴，大力发展托幼一体服务。
+- **安全生产与社会治理**：深入实施`安全生产治本攻坚三年行动`，抓好校园学生餐、平台外卖安全监管；推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国。
 # 重点工作
 ## 大力提振消费、提高投资效益，全方位扩大国内需求
-- **提振消费专项行动**：制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力，多渠道促进居民增收
-- **消费品以旧换新**：安排超长期特别国债**3000亿元**支持消费品以旧换新
-- **扩大服务消费**：扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力
-- **消费者权益保护**：强化消费者权益保护，营造安心放心消费环境
-- **扩大有效投资**：发挥各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目、管好用好资金，坚决防止低效无效投资
-- **投资资金安排**：今年中央预算内投资已安排**7350亿元**，用超长期特别国债更大力度支持"两重"建设
-- **政府投资机制**：优化地方政府专项债券管理机制，支持和鼓励民间投资发展，让民间资本有更大发展空间
+- **提振消费专项行动**：制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力，多渠道促进居民增收。
+- **消费品以旧换新**：安排超长期特别国债**3000亿元**支持消费品以旧换新，扩大健康、养老、托幼、家政等多元化服务供给。
+- **新型消费**：加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力，强化消费者权益保护。
+- **扩大有效投资**：发挥各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目、管好用好资金，坚决防止低效无效投资。
+- **投资规模**：今年中央预算内投资已安排**7350亿元**，用超长期特别国债更大力度支持"两重"建设，优化地方政府专项债券管理机制。
+- **民间投资**：支持和鼓励民间投资发展，让民间资本有更大发展空间。
 ## 因地制宜发展新质生产力，加快建设现代化产业体系
-- **培育新兴产业和未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动，培育生物制造、量子科技、具身智能、6G等未来产业
-- **产业统筹布局**：加强产业统筹布局和产能监测预警，梯度培育创新型企业，让更多企业在新领域新赛道跑出加速度
-- **传统产业改造升级**：深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型，开展标准提升引领传统产业优化升级行动，打造名品精品经典产业
-- **数字经济创新**：持续推进"人工智能+"行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展
+- **新兴产业和未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动，培育生物制造、量子科技、具身智能、6G等未来产业。
+- **产业统筹布局**：加强产业统筹布局和产能监测预警，梯度培育创新型企业，让更多企业在新领域新赛道跑出加速度。
+- **传统产业改造升级**：深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型，开展标准提升引领传统产业优化升级行动，打造名品精品经典产业。
+- **数字经济**：持续推进"人工智能+"行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展。
 ## 深入实施科教兴国战略，提升国家创新体系整体效能
-- **高质量教育体系建设**：制定实施教育强国建设三年行动计划，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育，扎实推进优质本科扩容，加快"双一流"建设
-- **教师队伍建设**：建设高素质专业化教师队伍，加强师德师风建设，推进教育改革发展，加快从教育大国向教育强国迈进
-- **科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革
-- **产学研深度融合**：加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目，健全科技成果转化支持政策和市场服务
-- **创新环境营造**：加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境
-- **人才队伍建设**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革，鼓励各类人才潜心钻研、厚积薄发
+- **高质量教育体系**：制定实施教育强国建设三年行动计划，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育，扎实推进优质本科，加快"双一流"建设。
+- **教师队伍建设**：建设高素质专业化教师队伍，加强师德师风建设，推进教育改革发展，加快从教育大国向教育强国迈进。
+- **科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革，加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目。
+- **科技成果转化**：健全科技成果转化支持政策和市场服务，加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境。
+- **人才队伍建设**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革，鼓励各类人才潜心钻研、厚积薄发。
 ## 推动标志性改革举措加快落地，更好发挥经济体制改革牵引作用
-- **国有企业改革**：高质量完成国有企业改革深化提升行动
-- **民营经济发展**：扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动
-- **政府服务企业**：政府要寓管理于服务之中，用服务的暖心增强企业的信心
-- **全国统一大市场建设**：纵深推进全国统一大市场建设，破除地方保护和市场分割，综合整治"内卷式"竞争，修订出台新版市场准入负面清单，优化新业态新领域市场准入环境
-- **市场制度完善**：构建统一的信用修复制度，完善企业简易注销程序，逐步推广经营主体活动发生地统计
-- **财税金融体制改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方
-- **资本市场改革**：深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设
+- **国企改革**：高质量完成国有企业改革深化提升行动，坚持和落实"两个毫不动摇"。
+- **民营经济**：扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动。
+- **营商环境**：政府要寓管理于服务之中，用服务的暖心增强企业的信心。
+- **全国统一大市场**：纵深推进全国统一大市场建设，破除地方保护和市场分割，综合整治"内卷式"竞争，修订出台新版市场准入负面清单，优化新业态新领域市场准入环境，构建统一的信用修复制度，完善企业简易注销。
+- **财税金融改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方，深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设。
 ## 扩大高水平对外开放，积极稳外贸、稳外资
-- **稳定对外贸易**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设，拓展境外经贸合作区功能
-- **贸易创新发展**：支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点
-- **吸引外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，加强外资企业服务保障
-- **自贸试验区建设**：推动自贸试验区提质增效和扩大改革任务授权，持续营造市场化、法治化、国际化一流营商环境
-- **共建"一带一路"**：统筹推进重大标志性工程和"小而美"民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局
-- **多双边和区域经济合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制，扩大同各国利益的汇合点
+- **稳定对外贸易**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设，拓展境外经贸合作区功能，支持内外贸一体化发展。
+- **服务贸易**：推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点。
+- **鼓励外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，加强外资企业服务保障，推动自贸试验区提质增效和扩大改革任务授权，持续营造市场化、法治化、国际化一流营商环境。
+- **共建"一带一路"**：推动高质量共建"一带一路"走深走实，统筹推进重大标志性工程和"小而美"民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局。
+- **多双边合作**：深化多双边和区域经济合作，持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制，扩大同各国利益的汇合点。
 ## 有效防范化解重点领域风险，牢牢守住不发生系统性风险底线
-- **房地产市场止跌回稳**：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，有序搭建相关基础性制度
-- **房地产发展新模式**：加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子
-- **地方政府债务风险化解**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，完善政府债务管理机制，坚决遏制违规举债行为
-- **金融领域风险防范**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险
-- **金融监管体系**：健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案，有效维护金融安全稳定
+- **房地产市场**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，有序搭建相关基础性制度，加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子。
+- **地方政府债务**：稳妥化解地方政府债务风险，完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，完善政府债务管理机制，坚决遏制违规举债行为。
+- **金融风险**：积极防范金融领域风险，一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险，健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案，有效维护金融安全稳定。
 ## 着力抓好"三农"工作，深入推进乡村全面振兴
-- **粮食稳产保供**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广
-- **粮食安全责任**：各地区都要扛稳保障国家粮食安全责任，共同把饭碗端得更牢
-- **巩固脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫，加强易地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度
-- **帮扶制度完善**：统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系
-- **农村改革发展**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围
-- **乡村产业发展**：因地制宜推动兴业、强县、富民一体发展，拓宽农民增收渠道，持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村
+- **粮食安全**：持续增强粮食等重要农产品稳产保供能力，稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广。
+- **粮食安全责任**：各地区都要扛稳保障国家粮食安全责任，共同把饭碗端得更牢。
+- **巩固脱贫成果**：毫不松懈巩固拓展脱贫攻坚成果，提高监测帮扶效率，确保不发生规模性返贫致贫，加强易地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分层分类帮扶制度，完善过渡期后帮扶政策体系。
+- **农村改革**：扎实推进农村改革发展，有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围，因地制宜推动兴业、强县、富民一体发展，拓宽农民增收渠道，持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村。
 ## 推进新型城镇化和区域协调发展，进一步优化发展空间格局
-- **农业转移人口市民化**：深入实施新型城镇化战略行动，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务
-- **公共服务保障**：强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道
-- **城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市
-- **区域战略实施**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极
-- **区域协同发展**：支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东、中、西、东北地区产业协作
+- **新型城镇化**：深入实施新型城镇化战略行动，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务，强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道。
+- **城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市。
+- **区域战略**：加大区域战略实施力度，发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极，支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东、中、西、东北地区产业协作。
 ## 协同推进降碳、减污、扩绿、增长，加快经济社会发展全面绿色转型
-- **污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程，积极推进美丽中国先行区建设
-- **绿色低碳经济发展**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用，健全绿色消费激励机制
-- **碳达峰碳中和**：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度，加快建设"沙戈荒"新能源基地
-- **煤电低碳化改造**：开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理
+- **污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程，积极推进美丽中国先行区建设。
+- **绿色低碳经济**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用，健全绿色消费激励机制，推动形成绿色低碳生产方式和生活方式。
+- **碳达峰碳中和**：积极稳妥推进碳达峰碳中和，建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度，加快建设"沙戈荒"新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理。
 ## 加大保障和改善民生力度，提升社会治理效能
-- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换
-- **就业创业服务**：优化就业创业服务，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障，开展大规模职业技能提升培训行动
-- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程，优化药品集采政策，强化质量评估和监管
-- **药品和医保**：健全药品价格形成机制，支持创新药发展，完善中医药传承创新发展机制，加强疾病预防控制体系建设，严格医保基金监管，让每一分钱都用于增进人民健康福祉
-- **社会保障**：城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金，推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、康复辅助器具购置和租赁支持力度
-- **生育支持**：制定促进生育政策，发放育儿补贴，大力发展托幼一体服务
-- **社会救助**：完善分层分类社会救助体系，保障困难群众基本生活
-- **精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业，推动优质文化资源直达基层，健全文化产业体系和市场体系
-- **全民健身**：推进群众身边的运动场地设施建设，广泛开展全民健身活动，加强青少年科学健身和健康干预，让年轻一代在运动中强意志、健身心
-## 维护国家安全和社会稳定
-- **公共安全治理**：深入实施安全生产治本攻坚三年行动，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对
-- **基层治理**：推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国
-- **"十五五"规划编制**：今年将开展"十五五"规划编制工作，科学确定发展目标，谋划好重大战略任务、重大政策举措、重大工程项目，更好发挥规划对经济社会发展的引领指导作用
+- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换，优化就业创业服务，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障，开展大规模职业技能提升培训行动。
+- **就业导向**：让多劳者多得、技高者多得、创新者多得。
+- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程，优化药品集采政策，强化质量评估和监管，健全药品价格形成机制，支持创新药发展，完善中医药传承创新发展机制，加强疾病预防控制体系建设，严格医保基金监管，让每一分钱都用于增进人民健康福祉。
+- **社会保障**：城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金，推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、康复辅助器具购置和租赁支持力度。
+- **生育支持**：制定促进生育政策，发放育儿补贴，大力发展托幼一体服务，完善分层分类社会救助体系，保障困难群众基本生活。
+- **精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业，推动优质文化资源直达基层，健全文化产业体系和市场体系，推进群众身边的运动场地设施建设，广泛开展全民健身活动，加强青少年科学健身和健康干预。
+- **国家安全和社会稳定**：全面贯彻总体国家安全观，完善公共安全治理，深入实施安全生产治本攻坚三年行动，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对，推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国。
 ## 政府自身建设
-- **法治政府建设**：严格依照宪法法律履职尽责，自觉接受同级人大及其常委会的监督、人民政协的民主监督、社会和舆论的监督，加强审计监督
-- **行政效能提升**：善于把党中央决策部署和自身实际结合起来，提高创造性贯彻落实能力，切实把面向基层的督查检查考核减下来，让广大干部把更多时间和精力用到干实事上
-- **廉政建设**：深入贯彻中央八项规定精神，坚定不移推进政府党风廉政建设和反腐败斗争，政府工作人员要恪尽职守、廉洁奉公、依法办事，确保党和人民赋予的权力始终用来为人民服务
-## 国防、港澳台与外交工作
-- **国防和军队建设**：深入贯彻习近平强军思想，贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全面深入贯彻军委主席负责制，全力打好实现建军一百年奋斗目标攻坚战，深入推进练兵备战，协力推进跨军地改革
-- **港澳工作**：全面准确、坚定不移贯彻"一国两制"、"港人治港"、"澳人治澳"、高度自治的方针，维护宪法和基本法确定的特别行政区宪制秩序，落实"爱国者治港"、"爱国者治澳"原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局
-- **对台工作**：坚持贯彻新时代党解决台湾问题的总体方略，坚持一个中国原则和"九二共识"，坚决反对"台独"分裂和外部势力干涉，推动两岸关系和平发展，完善促进两岸经济文化交流合作机制和政策，坚定不移推进祖国统一大业
-- **外交工作**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，推动落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体</t>
+- **十五五规划编制**：今年将开展"十五五"规划编制工作，科学确定发展目标，谋划好重大战略任务、重大政策举措、重大工程项目，更好发挥规划对经济社会发展的引领指导作用。
+- **法治政府建设**：严格依照宪法法律履职尽责，自觉接受同级人大及其常委会的监督、人民政协的民主监督、社会和舆论的监督，加强审计监督。
+- **行政效能**：善于把党中央决策部署和自身实际结合起来，提高创造性贯彻落实能力，切实把面向基层的督查检查考核减下来，让广大干部把更多时间和精力用到干实事上。
+- **廉政建设**：深入贯彻中央八项规定精神，坚定不移推进政府党风廉政建设和反腐败斗争，全面提升政府履职能力，确保党中央决策部署不折不扣落实到位。</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10273/7576</t>
+          <t>10273/7559</t>
         </is>
       </c>
     </row>
@@ -12385,66 +12269,71 @@
       <c r="C34" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为景城苑小区物业招标答疑会，由业主代表（主持人）与两家物业公司（富家物业、资平物业）就小区改造、停车管理、承接查验、安防整改等问题进行问答，最终由评标委员会打分确定中标单位。
-富家物业承诺一年内完成改造，并提出具体措施：针对停车乱象先分析原因（场地不足或业主不自觉）再制定对策；承接查验提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先与原物业私下沟通，解决不了则请业委会或街道社区协调，必要时在许可下采取强制措施；安防整改包括大门口增设人行门禁系统（支持微信、卡、密码）、大堂报到系统升级、地面增设隔离墩、外围停车场建设并安装停车管理系统、小区内增设电动车停车场。
-资平物业介绍公司背景（成立于2004年，总部深圳，全国367个项目，127个业委会项目，创始人陈志平原为万科物业创始人，中国物业管理协会副会长单位、全国百强企业），团队编制16人，薪酬福利高于周边同类项目，一线人员全部直招不外包；进场第一个月调动湖南战队资源进行环境绿化清洁整改，设备设施问题由集团设备公司工程师全面排查，合理范围内集中改造，重大改造需业委会授权或业主大会招投标，八个月内完成设备设施和现场整改；导入顾客管理系统集中处理业主投诉、咨询、报事，根据大数据分析业主投诉指导下月工作重点，每两个月开展一次社区文化活动；包干制经验：湖南11个项目，10个包干制，1个酬金制。
-评标结果：深圳市资平物业发展有限公司中标（第一名），第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居基业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。打分环节全程保密，暂停网络直播，录像材料不予公开，去掉一个最高分和一个最低分。
+景城苑小区物业招标答疑与评标会由业委会组织，富家物业与知名管理两家物业公司先后应答业主提问，最终经评标委员会打分，深圳市资平物业发展有限公司中标。会议围绕小区改造方案、车辆停放与安防管理、承接查验与交接、包干制经验、楼层杂物处置等议题展开，两家公司分别提出一年内完成12大改造点、四步举措（洗理静音、疏金活选、疑难杂症、有效提升）等整改计划。评标结果：第一名深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居基业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分；打分环节全程保密，暂停网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。
 # 分段速览
-## 00:00:10-00:09:36 富家物业答疑
-业主代表开场说明可自由提问，随后就小区改造、停车管理、承接查验、安防整改、满意度提升等五个方面向富家物业代表提问。富家物业代表逐一回应：改造项目已在标书117页详细说明，预计一年内完成；停车乱象先分析原因再制定对策；承接查验提前两周项目负责人入场摸底、提前一周服务人员到位培训；安防整改提出五项具体措施；管理方法概括为「用心倾听、如实记录、马上处理、及时反馈」。
+## 00:00:10-00:09:25 富家物业答疑
+业主代表开场说明可自由提问，随后就富家物业提出五个问题。富家物业代表逐一回应：改造项目已由林总介绍12大改造点，详见标书117页，预计一年内完成；针对卫生室车辆乱停，先分析原因是场地不足还是业主不自觉，再分别采取增加停车位或保安客服现场劝导措施；承接查验方面，提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先与物业私下沟通，再请业委会或街道社区协调，必要时在许可下采取强制措施；
+安防与停车管理提出增设人行门禁、升级大堂报到系统、增设隔离墩、建设外围停车场、增设电动车停车场五项措施；管理上采取"用心倾听、如实记录、马上处理、及时反馈"四句话方法。
 ## 00:09:36-00:11:56 评标流程说明
-业主代表宣布下一家投标公司为深圳市资平物业发展有限公司，并说明抢标时间为10分钟、每道答题时间3分钟。期间有短暂的人员沟通与准备环节。
-## 00:11:56-00:19:44 资平物业公司介绍与改造计划
-资平物业代表从四个方面汇报：公司成立于2004年，总部在深圳，全国367个项目、127个业委会项目，创始人陈志平原为万科物业创始人；管理理念为「一线权利归还业主」，财务与管理透明；团队编制16人，薪酬福利高于周边同类项目，一线人员全部直招不外包；进场后分四步推进——第一个月环境绿化集中整改、设备设施全面排查、八个月内完成重大改造、导入自身管理标准与顾客管理系统，每两个月开展一次社区文化活动。
-## 00:19:44-00:34:44 资平物业答疑
-业主代表就改造措施与时限、包干制经验与公益性服务、承接查验安排、安防与停车整改、楼层杂物堆放等五个问题提问。资平物业代表回应：进场一个月完成环境整改，半年内处理设备设施，一年内保证小区有序运转；湖南11个项目中10个为包干制，强调财务透明与业主知情权，提供居家上门、家政、24小时护送等有偿无偿服务；承接查验分专业组进行，增派150%人员；安防整改从关键岗位老员工值守、停车管理方案、技术手段三方面入手；楼层杂物以宣传引导、联合社区、疏导为主，不采取强制措施，并计划设置集中晾晒区。
-## 00:34:44-00:35:28 评标与结果公布
-业主代表宣布评标委员会打分，打分环节全程保密、暂停网络直播、录像材料不予公开，去掉一个最高分和一个最低分。最终公布结果：第一名中标候选人为深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居基业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。
+业主代表宣布下一家投标公司为深圳市资平物业发展有限公司，并说明抢标时间10分钟、每道题答题时间3分钟。期间有简短交流，确认题目编号为1213。
+## 00:12:22-00:19:44 知名管理公司介绍与答疑
+知名管理公司代表介绍公司背景：成立于2004年，总部深圳，全国367个项目（127个业委会项目），创始人陈志平原为万科物业创始人，公司为中国物业管理协会副会长单位、全国百强企业。团队编制16人，薪酬福利高于周边同类项目，一线人员不外包。提出四步举措：洗理静音（第一个月环境绿化清扫）、疏金活选（设备设施排查诊断）、疑难杂症（重大改造需业委会授权）、有效提升（导入管理标准），半年到八个月保证项目有效运作。导入顾客管理系统集中处理业主投诉咨询，每两个月开展一次社区文化活动。
+## 00:19:52-00:34:44 知名管理公司答疑
+业主代表就五个问题提问，知名管理公司代表逐一回应：改造方面，进场一个月集中整改环境绿化与卫生，半年内完成设备设施排查，八个月内达到有序状态；包干制方面，长沙11个项目中有10个包干制，保证财务透明、管理透明，团队30%为现有干部、60%为优秀员工或新招聘，公益服务包括居家上门免费人工、家政及24小时护送；承接查验方面，前期与社区街道派出所沟通、与业委会和原物业明确设备设施及债务债权，按专业线分组并增派150%人员；
+安防方面，关键岗位用老员工、收集业主车辆信息制定停车管理方案、通过技术手段加强监控；楼层杂物方面，以宣传引导、联合社区应急管理部门、上门沟通限期处理、设置临时堆放区等方式疏导，并规划集中晾晒区。
+## 00:35:00-00:35:33 评标结果公布
+业主代表宣布评标委员会打分，打分环节全程保密，暂停网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。公布结果：第一名中标候选人为深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居基业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。招标活动圆满结束。
 # 要点梳理
 ## 富家物业答疑
-- **改造项目与时限**：富家物业承诺中标后一年内完成系列改造，具体12大改造点已在标书117页详细说明。
-- **停车乱象应对**：先分析乱停原因（场地不足或业主不自觉），停车位不够则增加停车位；业主不自觉则派保安、客服现场说服、劝阻、纠正。
-- **承接查验准备**：提前两周项目负责人入场摸底小区现场情况；提前一周服务人员全部到位并培训公司制度与操作流程。
-- **交接不畅应对**：先与原物业私下沟通了解诉求，公司间能解决则直接解决；解决不了则请业委会或街道社区组织现场协调会；仍无法解决时，在业委会、业主大会及街道社区许可下采取强制措施。
-- **安防整改措施**：大门口增设人行门禁系统（支持微信、卡、密码进出）；大堂报到系统升级，业主车辆信息统一录入管理，临时车辆由安保登记放行并询问。
-- **停车管理整改**：地面增设隔离墩，禁止公共场所停车，保障消防通道与人行通道畅通；外围停车场建设并安装停车管理系统；小区内增设电动车停车场（考察发现电动车乱停与停车位不足有严重关系）。
-- **业主服务方法**：采取「用心倾听、如实记录、马上处理、及时反馈」四句话原则，处理完成后及时向业主反馈完成时间，业主可联系确认。
-## 资平物业答疑
-- **公司背景**：资平物业成立于2004年，总部深圳，全国367个项目，其中127个业委会项目；创始人陈志平原为万科物业创始人，曾协同建立中国第一个业委会。
-- **行业资质**：中国物业管理协会副会长单位、全国百强企业；业务涉及社会公司及循环养老。
-- **管理理念**：打造「让一线权利归还业主」，所有业委会项目财务透明，包干制每季度公示物业管理费、停车费等财务数据；管理透明，业主可参与电梯、消防、外包等公共事务管理。
-- **团队配置**：景城苑项目团队编制16人，薪酬福利保证高于周边同类项目；一线人员全部直招不外包（长沙项目有外包影响服务品质的经验教训）。
-- **进场改造四步**：第一步「洗理静音」——进场第一个月调动湖南战队其他项目人员资源，对小区环境、绿化、清洁、杂物全面清扫，保证感官上干净整洁有序。
-- **设备设施整改**：第二步「疏金活选」——调动集团设备公司水电、给排水、电梯、消防工程师全面排查诊断，合理投资范围内集中改造；重大改造（消防、渗水等）需业委会授权或业主大会招投标。
-- **整改时限**：八个月以内完成设备设施及现场整改，保证项目有效运作；第四步「有效提升」——将总部管理标准与前沿管理经验延续至本项目。
-- **顾客管理系统**：全面导入顾客管理系统，集中处理业主投诉、咨询、报事，保证有人跟进、有人回访；根据每月业主投诉大数据指导下月工作重点（如10月保安门岗管控投诉多，11月重点改善）。
-- **社区文化活动**：针对小区老龄化导入适老活动（教老年人发抖音、服装帽林打造）；按小区不同团体（跳舞、打篮球）开展社区文化活动，公司硬性标准为每两个月开展一次。
-- **包干制经验**：湖南11个项目中10个为包干制、1个酬金制；包干制同样保证财务透明与业主知情权，形成信任关系；团队管理干部30%来自现有优秀员工，60%左右为现有物业优秀员工或重新招聘。
-- **公益性服务**：长沙项目居家上门服务员工免费，材料费由业主自买或物业代购；开展家政、24小时业主护送服务等有偿与无偿业务。
-- **承接查验安排**：前期与社区街道、派出所沟通，与现有物业及业委会明确设备设施、债务债权；按专业线分专业组，委派集团工程师协助查验，避免消防、漏电、监控门禁等遗留问题。
-- **承接查验人员增派**：现有16人团队基础上增派150%人员，有成熟的标准建立与承接查验小组，确保交接问题能准确查出、不留隐患。
-- **安防与停车管理**：门岗、门勤岗、车务岗等关键岗位由老员工担任，对外来人员车辆进行管控、登记、核实后放行；收集业主车辆信息，制定整体停车管理方案（含禁区停放、动线管理），形成小区停车制度公约。
-- **技术手段应用**：利用自有设备公司与平台，通过技术手段解决关键部位监控、停车管控问题，识别外来人员与业主亲属来访。
-- **楼层杂物处理**：宣传引导为主，上门宣传与海报宣传法律知识及风险责任；与社区、应急管理部门联合行动；提前沟通并给业主处理杂物的时间段。
-- **杂物疏导方案**：物业可提供闲置区域供业主临时堆放杂物（贴纸条注明临时存放、限期解决），以疏导而非强制方式避免激发矛盾。
-- **晾晒问题解决**：在小区寻找位置设置集中晾晒区供业主晒被子；部分项目可提供增值服务——太阳大时物业工作人员免费上门取送晾晒物品（提前预约，早上拉出晚上拉回）。
+- **改造项目与时间**：富家物业林总已介绍12大改造点，详细说明在标书117页，预计改造时间一年内完成。
+- **卫生室车辆停放问题**：业主指出卫生室存在车辆停放不规范、电动车乱停现象；富家物业回应先分析原因（停车场地不够、业主觉得远、不自觉），再制定对策。
+- **停车问题应对措施**：若停车位不够则增加停车位；若业主不自觉，派保安、客服人员现场说服、劝阻、纠正，引导业主按规定停放。
+- **承接查验准备**：富家物业有丰富二手小区交接经验；提前两周项目负责人入场摸底，提前一周服务人员安排到位并培训，了解公司制度和操作流程。
+- **交接不畅应对**：先与原物业私下沟通了解诉求；公司间无法解决时，请业委会或街道社区组织现场协调会；仍无法解决时，在业委会、业主大会及街道社区许可下采取强制措施。
+- **安防与停车管理**：大门口增设人行门禁系统（微信、卡、密码进出）；大堂报到系统升级，录入业主车辆信息统一管理，临时车辆由安保登记放行。
+- **停车管理措施**：地面增设隔离墩，禁止公共场所停车，保证消防通道和人行通道畅通；建设外围停车场并安装停车管理系统；小区内增设电动车停车场（因景盛苑小区电动车停车场不足）。
+- **类似项目管理经验**：富家物业表示没有与景城苑很相似的小区，每个小区有具体情况。
+- **业主反馈处理**：采取四句话方法——用心倾听、如实记录、马上处理和及时反馈，处理完成后向业主反馈完成时间。
+## 知名管理公司介绍与答疑
+- **公司背景**：知名管理成立于2004年，总部深圳，全市场化物业公司（无开发背景）；全国367个项目，其中127个业委会项目。
+- **创始人渊源**：公司创始人陈志平先生原为万科物业创始人，在深圳从事物业管理时协同建立中国第一个业委会。
+- **行业地位**：中国物业管理协会副会长单位、全国百强企业。
+- **团队配置**：景城苑项目人员编制16人，薪酬福利保证高于周边同类项目；所有一线人员直招不外包。
+- **四步举措**：洗理静音（进场第一个月调动湖南战队资源，对绿化清洁、杂物全面清扫）；疏金活选（调动设备公司水电、给排水、电梯、消防工程师全面排查诊断设备设施）。
+- **四步举措（续）**：疑难杂症（涉及消防、渗水等重大改造，检查后提供意见，经业委会授权或业主大会招投标）；有效提升（导入总部管理标准和前沿管理经验）。
+- **改造时间计划**：半年到八个月以内完成设备设施和现场整改，保证项目有效运作；一年内保证小区达到有序状态。
+- **顾客管理系统**：全面导入顾客管理系统，集中处理业主投诉、咨询、报事，保证有人跟进、有人回访；根据每月投诉报事数据形成大数据库，指导下月工作方向。
+- **社区文化活动**：针对小区老龄化导入巡产活动，教老年人使用抖音等；根据小区不同团体（跳舞、打篮球等）做社区社团；公司硬性标准为每两个月开展一次社区文化活动。
+- **包干制经验**：长沙11个项目，其中10个包干制、1个酬金制；包干制下保证财务透明（每季度公示物业管理费、停车费）和管理透明（业主参与公共事务管理）。
+- **团队组建**：管理干部30%从集团现有人员选拔，60%左右包括现有物业优秀员工及重新招聘，保证团队整体优秀。
+- **公益性服务**：长沙项目居家上门服务员工免费，材料费由业主自买或物业代购；开展家政、24小时业主护送服务等有偿和无偿业务。
+- **承接查验准备**：前期与社区街道、派出所沟通；与现有物业、业委会坐下来明确设备设施、债务债权等事项。
+- **承接查验专业性**：按不同专业线分专业组，调动集团工程师协助项目查出问题；与物业、业委会妥善沟通，避免形成对立局面。
+- **承接查验人员增派**：在现有16人团队基础上增派150%人员，保证承接查验和数字化工作有成熟小组参与。
+- **安防人员管理**：门岗、门勤岗、车务等关键岗位由老员工担任，保证责任心和担当意识，对外来人员和车辆进行管控、登记、核实后放行。
+- **停车管理方案**：收集小区业主车辆信息，制定整体停车管理方案（含禁区停放）；道闸升级改造识别外来人员和业主亲戚来访；形成小区停车管理制度和公约。
+- **监控技术手段**：通过自身设备公司和平台，在技术层面解决关键岗位和关键部位监控问题。
+- **楼层杂物处理**：宣传引导为主，通过上门宣传、海报重复宣传法律知识，让业主明白堆放杂物的风险和法律后果；与社区应急管理部门联合行动。
+- **杂物疏导措施**：与业主全面沟通，告知危害并给出处理时间段；物业可提供闲置小区域供业主临时堆放（贴纸条注明临时存放、限期解决），以疏为主、不强制。
+- **晾晒问题处理**：在小区寻找位置建集中晾晒区供业主晒被子；太阳大时物业工作人员可上门免费提供晾晒增值服务（提前预约，早上拉出、晚上拉回）。
 ## 结论与决定
-- **中标结果**：深圳市资平物业发展有限公司为第一名中标候选人，中标景城苑小区物业项目。
-- **评标得分**：第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居基业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。
-- **打分规则**：评标打分去掉一个最高分和一个最低分；打分环节全程保密，暂停网络直播，录像材料不予公开。
+- **评标结果**：第一名中标候选人为深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居基业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。
+- **打分规则**：总评委打分去掉一个最高分和最低分；品牌质量需三个评委签名。
+- **保密要求**：打分环节全程保密，暂停会场网络直播，录像材料不予公开；除评委、监督员及必要会务人员外，其余人员退场。
 ## 待确认与风险
-- **监控门禁失效**：小区存在监控门禁失效问题，导致人员车辆随意进出。
-- **停车管理混乱**：小区内停车管理混乱，存在车辆乱停现象，含消防通道停车问题。
-- **楼层杂物风险**：楼层顶层存在堆放杂物或乱搭乱晒问题，处理不当可能激发矛盾。
-- **交接不畅风险**：与原物业交接不畅可能导致承接查验困难，需提前准备应对措施。</t>
+- **卫生室车辆停放**：存在车辆停放不规范、电动车乱停现象，需分析原因后制定对策。
+- **小区安防**：监控门禁失效，导致人员和车辆随意进出。
+- **停车管理**：小区内停车管理混乱，消防通道停放车辆（含业主车辆和外来车辆）。
+- **楼层杂物**：楼层顶层存在堆放杂物、乱搭乱晒问题，需在不激发矛盾前提下疏导解决。
+- **交接风险**：承接查验若交接不畅，可能导致后续遗留问题；需通过专业分组查验避免遗漏。</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>57.9</v>
+        <v>63</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11743/4066</t>
+          <t>11743/4015</t>
         </is>
       </c>
     </row>
@@ -12567,60 +12456,46 @@
       <c r="C35" t="inlineStr">
         <is>
           <t># 讲座概况
-本期视频由主讲人李正讲述康熙朝文渊阁大学士陈廷敬的一生，主题聚焦于其生平事迹与品格，形式为历史讲述视频。李正开篇即指出，影视剧中陈廷敬支持撤藩、招抚台湾、征剿噶尔丹等功绩均非史实，但康熙临终前仍询问大臣中是否有学问人品如陈廷敬者可代理内廷事务，足见其重要性。讲座面向对清代历史、人物传记感兴趣的观众，旨在通过陈廷敬的一生展现清廉正直的为官之道。
-讲座围绕陈廷敬人生的三个阶段展开：**母亲张氏的开蒙**、**圣祖康熙的讲师**、**至公无私的落幕**。核心主张有二：其一，陈廷敬虽无影视剧中的显赫功绩，却凭借清廉自守与恪守初心赢得康熙终身信任；其二，其一生印证了《论语》中“苟正其身矣，于从政乎何有”的道理。关键锚点包括：陈廷敬**21岁中进士入翰林**、**75岁病逝谥号文贞**、康熙赐匾额“午亭山村”及楹联“春归乔木浓阴茂，秋到黄花晚节香”。对听众而言，陈廷敬“知世故而不世故”的处世态度与铁面无私的为官风格，对理解清代官场生态及个人品格修养均有启示意义。
+本期视频由主讲人李正讲述康熙朝文渊阁大学士、总理南书房大臣陈廷敬的一生，按**母亲张氏的开蒙、圣祖康熙的讲师、至公无私的落幕**三个阶段展开。李正开篇即指出，影视剧中陈廷敬支持撤藩、招抚台湾、征剿噶尔丹等功绩均非史实，但康熙临终前仍询问大臣中是否有学问人品如陈廷敬者可代理内廷事务，足见其分量。核心主张有三：其一，陈廷敬的童年教育主要由母亲张氏完成，6岁前已口授背诵《论语》《孟子》《大学》《中庸》《诗经》；其二，他以日讲官、经筵讲师身份与康熙朝夕相处，教学风格外放、三观坚定；其三，他一生清廉，历经亲家张谦攀咬案后仍获康熙信任，宦海浮沉50年声名清白。关键锚点包括：**21岁中进士入翰林**、**康熙临终问询**、**谥号文贞**。对听众而言，本讲以陈廷敬生平为镜，呈现「苟正其身矣，于从政乎何有」的为官之道。
 # 核心观点与论证
-## 论点：陈廷敬的童年开蒙由其母张氏主导，奠定其学术与品格根基
-- **家庭背景**：陈廷敬本名陈敬，字子端，号午亭，1638年（崇祯11年）出生于山西泽州府阳城县，家中六代皆为读书人，多在朝廷为官；其父陈长七为管理家业未走仕途，但入选过顺治朝国子监，史载“陈文征公考选拔贡生，好善乐义”。
-- **母亲张氏的学识**：张氏自幼随父张弘毅认真读书，通晓儒家经典与《资治通鉴》，陈廷敬形容“太夫人少儿颖慧特异”；嫁入陈家后每日干完家务即读书背诵，常至半夜不睡，史载“太夫人于家政稍暇即出书籍，平几装诵，非秉夜不归寝，经商好学者亦无以加也”。
-- **早期教育内容**：陈廷敬6岁外出上学前，已被母亲口授背完《论语》《孟子》《大学》《中庸》及《诗经》，史载“凡四子书毛诗皆太夫人口授以诵”。
-- **鼓励式教育**：陈廷敬9岁作诗《咏牡丹》，其中“要使误接春”一句获母亲张氏称赞“我儿子这就是天才”，体现张氏善于鼓励孩子。
-- **科举成绩**：顺治八年（1651年）陈廷敬14岁赴试潞安府，以全省第一考中秀才；随后20岁中举人，21岁中进士，同年入选翰林院任庶吉士——对比李光地21岁尚未考中秀才，可见其天赋。
-## 论点：陈廷敬入翰林后因重名改名，获顺治赐名“廷敬”，并凭教学才能成为康熙讲师
-- **重名风波**：顺治15年四月，陈廷敬与直隶通州学子陈敬同届中进士入翰林，因清朝政府文件满汉双语、庶吉士须学满文，直隶陈敬学不好满文被顺治点名批评并罚俸一年，但顺治未带籍贯，导致翰林院风言风语牵连陈廷敬。
-- **主动改名**：陈廷敬22岁时主动上书顺治奏请更名，史载“庶吉士陈敬奏请更名廷敬，以与直隶庶吉士陈敬同名故也”；据李光地记载，“廷”字为顺治所赐，原话“陈文贞公初名敬，其家廷字文选日张皇帝所赐也”。
-- **仕途起步**：顺治18年庶吉士毕业考试，24岁的陈廷敬考取同届第一，获授秘书院检讨；顺治与陈廷敬同年同岁（均生于崇祯11年），顺治颇为欣赏他，史载“陈文真公时若冠祥祥玉堂所一席之夜往往蒙上赞许”。
-- **为母请假归乡**：顺治18年年初顺治驾崩，康熙元年母亲张氏病倒，陈廷敬在仕途起步关键期请假归乡三年，史载“泽州陈文贞公，性至孝，时登极，闻太夫人病，即归省”；母亲病愈后，陈廷敬履历出现三年空白。
-- **重返官场**：康熙六年陈廷敬考察一等称职，两年后32岁升任正六品国子监司业（其父陈长七15年前还只是国子监学生，形成对父辈的超越）。
-- **整顿国子监**：当时国子监有不成文规定，学生拜见校长老师须带见面礼，陈廷敬拒绝收礼，史载“凡诸生以至献者悉秉去之”——学生越送礼越不见，不送礼才愿见；此举未受排挤，反而两年内连升三级，34岁官居从四品翰林院侍讲学士。
-- **成为康熙讲师**：康熙11年十月，35岁的陈廷敬充日讲起居注官；康熙15年九月，39岁以内阁学士兼礼部侍郎充经筵讲官；康熙16年正月出任翰林院长院学士，教习当届庶吉士。
-- **教学风格**：陈廷敬讲评经史“特别狠辣，对就骂错就骂，从不含糊其辞”，曾指着史书痛骂三国孙权背刺关羽，原话“无鼠相存，譬犹唇齿，不必智者而知之……全其屯权也哉”，斥孙权“简直就是猪是狗”。
-- **母亲去世与康熙破例**：康熙16年张氏病逝，终年59岁；康熙下令“满汉大臣俱系一体，汉大臣有丧，亦应遣大臣往次”，派大学士明珠、喇沙里携茶酒往祭；礼部以陈母封号系詹事任上所得、按例不得祭奠为由反对，康熙回应“以平靖世将握秦而恩福待，吾何以劝劳臣乎”，最终追封陈母按学士品级由官方祭奠。
-## 论点：陈廷敬任左都御史后整顿捐纳积弊，以考试筛选候补官员
-- **捐纳背景**：康熙12年三藩之乱爆发至康熙22年统一台湾，清政府连打十年仗，为筹军费开放捐纳，不少人花钱买官；陈廷敬上任左都御史时，吏部仍有大量捐纳者排队等分配岗位。
-- **上奏建议**：陈廷敬上奏称“自古未有不晓文艺之人可以为民父母者也”，主张捐纳者正式上岗时须追加考试，“文艺略小者给予录用，否则且令异业听其再试”。
-- **吏部反对与康熙支持**：吏部以“以前补用人员从未考试”为由反对；康熙支持陈廷敬，并补充令各地督抚详查已任命官员，“凡临民之官内有不识字义者，着该督府不时实行查参修治”。
-- **后续整顿**：陈廷敬针对各省督府作风问题、地方政府赈灾懒政问题严查弹劾，并亲自拟定新的赈灾报批流程；面对劝其“和光同尘”的声音，他表示“我贤与虽折且怨，庸和尚说只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，你也是无所谓的”。
-## 论点：张谦案中陈廷敬遭亲家攀咬，辞官自证清白后获康熙重新启用
-- **案件经过**：康熙26年，50岁的陈廷敬任工部、户部、吏部三部尚书期间，湖广巡抚张谦（陈廷敬老乡兼亲家，其子为陈廷敬二女婿）因贪污被抓，口供称曾贿赂陈廷敬、徐天学、高士奇，并拿出三人劝其好好当官的信件作为“索贿暗示”证据。
-- **陈廷敬自辩**：陈廷敬称从未收钱，原话“前楚府一案者，千随臣弃敬畏自分嫌疑之际……积疑成恨，羽射连染”，认为张谦因自己过于疏远而怨恨攀咬。
-- **康熙处置**：康熙传旨主审官马齐“此时需旧款需问，不可蔓延，若蔓延则千累者重，倘有别事，尔等既来密奏”，只处理张谦一人，其余密查；但密查反而无法尽快还陈廷敬清白。
-- **辞官自证**：51岁的陈廷敬主动上书辞官，原话“唯早夜静静私自淬砺，不寻亲党，不阿友朋……唯当隐退田间，永衔恩于高厚”；康熙准许辞官但留其在京修书。
-- **真相推测**：据李光地记载，陈廷敬后来吐槽张谦案从索贿到举报皆由徐乾学（徐东海）一手策划，原话“陈泽周演，再破张骞做巡抚，要银子也是徐东海……始终皆徐为之”；徐乾学、高士奇后来均因贪污被罢官，唯独陈廷敬康熙29年（53岁）复出再任左都御史，康熙以此宣告其清白。
-- **晚年仕途**：陈廷敬复出后历任一年刑部尚书、六年户部尚书、四年吏部尚书；康熙42年66岁升任文渊阁大学士，同时总理南书房事务，成为内阁中唯一既管南书房又任经筵讲师的大学士。
-## 论点：陈廷敬晚年多次请退，康熙始终挽留，最终以文贞谥号落幕
-- **请退过程**：康熙46年陈廷敬70岁起逐渐上书申请退休，康熙以“机务重地，良难其人。不必求去”拒绝；70岁、71岁、72岁连续三年三次申请均被拒。
-- **康熙挽留原因**：陈廷敬任大学士期间是内阁中唯一既管南书房又定期给康熙上课的经筵讲师；康熙49年，73岁的陈廷敬第四次申请退休终获准奏。
-- **御赐匾联**：康熙亲赐匾额“午亭山村”（陈廷敬自家宅名）与楹联“春归乔木浓阴茂，秋到黄花晚节香”，并说“朕特殊匾联赐卿，自此不与人写字矣”。
-- **身后哀荣**：两年后陈廷敬病逝，终年75岁，谥号文贞，史称陈文贞公；康熙包办全部治丧费用，从大内找紫砂碗做棺材，并下令各部院满汉大臣往吊，派皇三子允祉及大臣侍卫往祭。
-- **一生总结**：陈廷敬21岁入官场至75岁，宦海浮沉50余年声名清白；李正引用《论语》“苟正其身矣，于从政乎何有”作结，强调其儿时所学道理至死未违背。
+## 论点一：陈廷敬的早年教育与科举成就奠定其仕途基础
+- **母亲张氏开蒙**：陈廷敬6岁外出上学前，由母亲张氏口授背诵《论语》《孟子》《大学》《中庸》《诗经》四书及毛诗；张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，史载其"家政稍暇即出书籍，平几装诵，非秉夜不归寝"。
+- **科举成绩优异**：顺治八年（1651年）陈廷敬14岁以童子第一入州学；20岁中举人，21岁中进士，同年入选翰林院任庶吉士；顺治18年庶吉士毕业考试获同届第一，授秘书院检讨。
+- **改名获御赐**：顺治15年四月，因与直隶通州陈敬同名，陈廷敬奏请更名；据李光地记载，"廷"字为顺治所赐，借此与顺治拉近关系，顺治与陈廷敬同为崇祯11年出生。
+## 论点二：陈廷敬以清廉正直与教学才能获康熙信任
+- **国子监整顿**：康熙八年（1669年）陈廷敬32岁升任正六品国子监司业，废除学生拜见须带见面礼的不成文规定，"凡诸生以至献者悉秉去之"，学生越送礼越不见，两年内连升三级。
+- **经筵讲师**：康熙11年十月陈廷敬35岁充日讲起居注官，康熙15年九月39岁充经筵讲官；教学风格外放，讲评经史"对就骂错就骂"，曾指史书骂孙权"全其屯权也哉"，康熙欣赏其坚定三观。
+- **母亲丧礼破格**：康熙16年母亲张氏去世终年59岁，康熙下令满汉大臣一体、汉臣有丧亦遣大臣往祭，派明珠、喇沙里携茶酒往祭；礼部以陈母封号按詹事品级无资格祭奠反对，康熙坚持"以平靖世将握秦而恩福待，吾何以劝劳臣乎"，追封按学士品级祭奠。
+## 论点三：陈廷敬任左都御史后以整顿吏治为核心政绩
+- **捐纳者追加考试**：康熙23年陈廷敬47岁升任左都御史，上奏"捐纳买官买的只是候补资格，正式上岗时必须追加考试"；吏部反对，康熙支持并补充令各地督抚详查已任命官员，"凡临民之官内有不识字义者，着该督府不时实行查参修治"。
+- **全面弹劾整顿**：针对各省督府作风问题、地方政府赈灾懒政问题严查弹劾，一边指出问题一边给出解决方案，亲自拟定新的赈灾报批流程；此后连续出任工部、户部、吏部三部尚书，"他人到哪里就整顿到哪里"。
+- **张谦案风波**：康熙26年湖广巡抚张谦（陈廷敬亲家）贪污被抓，供称贿赂陈廷敬、徐乾学、高士奇，证据为三人曾写信劝其好好当官；陈廷敬辩称"张谦完全是因为自己对他过于疏远，反而产生了怨恨，在恶意攀咬自己"。
+## 论点四：张谦案后陈廷敬以清白复出并获康熙终身信任
+- **辞官自证清白**：康熙传旨主审官马齐"只处理张谦，不得蔓延，其他人密查"；陈廷敬51岁主动上书辞官，康熙准许但留京修书；康熙29年53岁复出再任左都御史，康熙以重新任命全国最高监察长官宣告其清白。
+- **李光地证词**：据李光地记载，陈廷敬曾吐槽"整个张谦案从索贿到举报，其实都是徐乾学一手策划"；徐乾学、高士奇后来均因贪污被罢官，唯独陈廷敬仅辞官一年即被重新启用。
+- **晚年高位与退休**：康熙42年陈廷敬66岁升任文渊阁大学士、总理南书房事务；70岁起连续三年申请退休均被康熙拒绝，康熙称"机务重地，良难其人"；康熙49年73岁第四次申请获准，康熙赐匾额"午亭山村"和楹联"春归乔木浓阴茂，秋到黄花晚节香"，并称"自此不与人写字矣"。
+- **身后哀荣**：两年后陈廷敬病逝终年75岁，谥号文贞；康熙包办治丧费用，从大内找紫砂碗做棺材，命皇三子允祉及大臣侍卫往祭，各部院满汉大臣往吊。
 # 金句总结
 &gt; 朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？
+- 康熙在陈廷敬临终前询问，是否有学问人品如陈廷敬者可代理内廷事务，足见其信任之深。
 &gt; 自古未有不晓文艺之人可以为民父母者也。
-&gt; 臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节。
+- 陈廷敬上奏捐纳者需考试时所言，强调父母官必须有文化素养。
+&gt; 我贤与虽折且怨，庸和尚说只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，你也是无所谓的。
+- 面对官场劝其圆滑处世的建议，陈廷敬表明自己坚持原则、不计较个人得失的立场。
 &gt; 苟正其身矣，于从政乎何有？
-&gt; 我贤与虽折且怨，庸和尚说只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，你也是无所谓的。
+- 李正引用《论语》总结陈廷敬一生，认为自身品行端正则治理政事无难事。
 &gt; 春归乔木浓阴茂，秋到黄花晚节香。
+- 康熙赐予陈廷敬的楹联，赞其一生干净、晚节不亏。
 # Q&amp;A 环节
 未提及</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>81.8</v>
+        <v>65</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9132/3630</t>
+          <t>9132/2175</t>
         </is>
       </c>
     </row>
@@ -13241,75 +13116,76 @@
       <c r="C36" t="inlineStr">
         <is>
           <t># 访谈概述
-本期《锵锵三人行》由窦文涛主持，邀请《明朝那些事儿》作者当年明月与嘉宾马先生，围绕日本历史剧《大奥》与明朝历史展开对谈。节目先讨论《大奥》所反映的日本文化，再转入明史研究难点、朱元璋评价、明朝兴亡经验及明式家具审美等话题，全程以中日文化差异为主线。
-关于日本文化，当年明月认为《大奥》是《大长今》之后更有影响的国外电视剧，其三部曲分别对应中国晚清到清初及明治维新前的时段。马先生指出大奥即后宫，日本话中“奥”指很深的地方；日本天皇是摆设，实际权力在幕府将军，德川家康开创德川幕府后权力集中。马先生强调日本人的极端精神——所有事情做到尽头，战后仅用30年成为世界第二经济强国（以绝对量计算），且是强国中唯一没有资源的国家。当年明月以豆腐厂为例说明日本人的一丝不苟：豆腐规定当天做当天卖，夜里11:45所有人待命，12点整开始干活，到4点多干完上市。日本实行终身雇佣制，但工作效率极高；日本文化强调忠诚，如阿福25岁进大奥当奶妈，65岁去世，40年不处于私心。
-关于明朝历史，当年明月解释自己写明史是因为明史资料最多；历史研究有两个难点，即先秦和明清，明史资料堆得比山高，但一个事件可能有七个不同说法。明朝260多年过程跌宕起伏，如土木堡之变、夺门之变。当年明月推崇朱元璋，因其从乞丐到皇帝，定下明朝规章制度且基本没有太大改动；朱元璋的好友汤和让他参加起义军，他因被告发被迫起义。马先生提到明朝仁宣盛世时间太短不怎么提，晚明时期市民生活特别轻松，想去哪去哪，皇册都不用了；江浙一带工商业兴起，给人当雇工活得很滋润；明末陕西发生大规模灾荒，李自成起义。当年明月引用“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，强调历史研究需设身处地。
-关于明式家具与审美，马先生解释宋明是典型的汉人政权，文人政权审美较高，满族是异族，对美的判断是表象的；今天凡是外在直观能看到的都卖得非常贵，而100年前晚清到民国初年，值钱的一定是素雅的。马先生提到天启皇帝爱当木匠，干完活拆大盆去卖，卖完还打听卖得怎么样，反映当时社会对家具的重视；明式家具在国际上地位高，不是偶然的。
+本期《锵锵三人行》由窦文涛主持，邀请《明朝那些事儿》作者当年明月与嘉宾马先生，围绕刚播完的日本历史剧《大奥》及明朝历史展开对谈。节目先讨论《大奥》所反映的日本文化，再转入明史研究难点、朱元璋评价、明朝兴亡经验及明式家具审美等话题。
+关于《大奥》，当年明月认为其影响力超过《大长今》，是近年来更有影响的国外电视剧。马先生解释“大奥”即后宫，日语中“奥”指很深的地方；日本天皇是摆设，实际权力在幕府将军，德川家康开创德川幕府后权力集中。当年明月指出日本文化具有“极端精神”，战后用30年成为世界第二经济强国（以绝对量计算），且是强国中唯一没有资源的国家；他以豆腐厂工人夜里12点整开始干活、4点多干完上市的实例，说明日本人的一丝不苟。窦文涛提到有人批评日本人的忠诚是“家奴”心态，马先生认为不能用另一标准评判。
+关于明朝历史，当年明月解释自己写《明朝那些事儿》是因为明史资料最多；历史研究有两大难点，一是先秦（史料少），二是明清（一个事件可能有七个不同说法）。他推崇朱元璋，认为他是历史上唯一由最底层（乞丐）当上皇帝的人，刘邦好歹是村长；朱元璋定下明朝规章制度，基本没有太大改动。马先生补充明朝260多年过程跌宕起伏，有土木堡之变、夺门之变；晚明江南工商业兴起，市民生活富裕，有文徵明、金瓶梅等。当年明月引用“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，强调历史教训不能直接套用。
+关于明式家具，马先生认为宋明是汉人文人政权，审美较高，对美的判断不是表象的；满族是异族，对美的判断是表象的，故宫大红大紫是满族趣味。他提到天启皇帝爱当木匠，干完活拆大盆去卖，卖得很好，反映当时社会对家具的重视；明式家具在国际上地位高不是偶然的。
 # 访谈详细记录
 ## 日本历史剧《大奥》与日本文化
-- **《大奥》反响**：当年明月认为《大奥》是《大长今》以后更有影响的国外电视剧，马先生与窦文涛均表示认同，认为该剧拍得非常好。
-- **《大奥》时代背景**：当年明月指出该剧三部曲中，前两部相当于中国晚清到清初时段，第三部在明治维新之前，是一部有跨越性的历史剧。
-- **大奥释义**：马先生解释大奥即后宫，日本话中“奥”指很深的地方，即屋子最里处，如“深奥”一词仍保留此痕迹。
-- **日本权力结构**：当年明月指出日本天皇一直是摆设，实际权力掌握在幕府将军手中；德川家康开创德川幕府后，日本所有权力集中在一人手上。
-- **天皇无实权史实**：当年明月提到曾研究日本战国历史，德川家掌权后天皇想举办活动但没钱，找将军要钱被拒，活动未办成；后来天皇为抗议幕府甚至退位。
-- **日本极端精神**：马先生认为从《大奥》可看出日本文化从头到尾没变，即一种“极端精神”——所有事情要做到尽头，每个人发自内心地认真。
-- **战后经济成就**：马先生强调日本战后1945年起用30年成为世界第二经济强国，以绝对量而非人均量计算，且是强国中唯一没有资源的国家，这不是偶然而是必然。
-- **中日文化差异**：当年明月认为中国文化精神是中庸，讲究融合之道；日本精神恰恰相反，坚持一个原则做到极致，如炮手忘记一切只记得开炮即达最高境界。
-- **忠诚文化**：马先生认为日本是忠诚文化的典型国家，多次赴日未感受到难过或非礼；窦文涛提到有批评称日本人的忠诚是“家奴”，马先生回应不能用另一标准评判。
-- **终身雇佣制**：马先生指出日本跳槽率最高，每次跳槽都是社会资源浪费；日本实行终身雇佣制，按经济学原理应导致低效，但日本终身雇佣下工作效率仍极高，是经济学上的奇迹。
-- **豆腐厂例子**：马先生讲述参观日本最底层豆腐厂经历：豆腐规定当天做当天卖，夜里11:45所有人做好不动手坐着看表，12点整开始干活，到4点多干完上市，期间无人闲聊。
-- **生存环境与团体规则**：当年明月认为日本没有资源、常火山地震，人对世界有极强求生欲望且悲观，必须融入团体按固定规则做事才能生存。
-- **聪明人无生存环境**：马先生认为日本社会文化抵制聪明人，耍滑者没有生存环境；举例日本做绳子做到全国第一的人，几年内不赚钱铺市场，最后靠各环节加2%利润赚大钱。
-- **阿福事例**：马先生以《大奥》中阿福为例说明日本忠诚文化：阿福25岁进大奥当奶妈，65岁去世，40年无论做什么事不处于私心、完全是公心，甚至被伤害的对方都认为她出于公心。
-- **慢慢来才是最快**：当年明月引用他人观点“慢慢来才是最快的方法”，认为每个人按自己角度做事最节省成本，不会互相抵消，形成合力非常可怕。
-- **日本人对死亡的态度**：当年明月认为日本人看樱花只看落的那天，因岛国生态环境恶劣，对死亡不是藐视而是有点向往或不惧怕；马先生反驳称日本民族不是藐视生命而是重视，经济危机时很多身家万贯者选择自杀。
-- **是否愿做日本人**：窦文涛问了解差异后是否愿做日本人，马先生认为每个人在自己文化环境里愿意做，但做不成，文化不允许这种现象生存；当年明月表示很不愿意，因为很多时候像盲从。
+- **《大奥》反响**：当年明月认为《大奥》是《大长今》以后更有影响的国外电视剧，马先生也认同，称其「拍得非常好」。
+- **剧情时段**：马先生介绍《大奥》共三部，前两部相当于中国晚清到清初时段，第三部在明治维新之前，是一部有跨越性的历史剧。
+- **「大奥」释义**：马先生解释「大奥」即普通话的「后宫」，日语中「奥」指很深的地方、屋子最里处，如「深奥」一词即保留此痕迹；大奥规矩严谨，后宫不许进人。
+- **日本权力结构**：当年明月指出日本天皇一直是摆设，实际掌权的是幕府将军；德川家康开创德川幕府后，日本所有权力集中在一人手上。
+- **天皇受冷落史实**：当年明月称曾研究日本战国历史，德川家掌权后天皇想办活动没钱、找将军要钱被拒，活动没办成；天皇为抗议幕府曾退位。
+- **中日对比**：当年明月对比称明朝皇帝为抗议可不上朝，但大臣仍听话、不敢造反；日本情况则是军人掌权，从唐朝开始一直是军人坐第一把交椅。
+- **日本极端精神**：当年明月认为《大奥》体现日本文化从头到尾没变，即「极端精神」——所有事情要做到尽头；战后1945年日本用30年成为世界第二经济强国（以绝对量计），且是强国中唯一没有资源的国家，这不是偶然而是必然。
+- **中庸与极端之别**：当年明月称中国文化精神是「中庸」，日本精神恰恰相反、坚持一个原则；他以马先生家具店中硬木刻云彩为例，称「这么硬的东西做得这么柔软」就是中庸——不是对错黑白之间，而是一条最适合的路。
+- **日本忠诚文化**：马先生称多次去日本未感到难过、无人非礼，文化差异从电视剧看得清楚，日本是「忠诚文化的典型国家」，强调坚韧不拔、做到极致与忠诚。
+- **对「家奴」批评的回应**：窦文涛提到有人批评日本人的忠诚是「家奴」心态，马先生回应称不能再用另一标准去评判，并举例日本跳槽率最高、每次跳槽都是社会资源浪费。
+- **终身雇佣制悖论**：当年明月称西方经济学无法理解日本——终身雇佣制缺乏竞争、按理效率极低，但日本终身雇用下效率仍特别高。
+- **豆腐厂实例**：马先生讲述参观日本最底层豆腐厂的经历：日本豆腐规定当天做当天卖，工人夜里11:45坐等看表，12点整准时开工，4点多干完上市，期间无人闲聊胡侃。
+- **生存环境与团体规则**：当年明月认为日本没有资源、常火山地震，人对世界有极强求生欲、甚至悲观，必须融入团体按固定规则做事才能生存；若有人偷奸耍滑坐收渔利，日本社会文化的抵制会让他很难过。
+- **做绳商人案例**：马先生举例日本做绳子的商人，几年内不赚钱、从批发到送货一分不赚，等市场铺平后拿进货单和卖价单各加2%，全国市场4%的利润就是不得了的数目。
+- **「慢慢来才是最快」**：当年明月称有人跟他讲过「慢慢来才是最快的方法」，所有人按自己角度做事最节省成本、不互相抵消，形成合力非常可怕。
+- **是否愿做日本人**：窦文涛问了解差异后是否愿做日本人；马先生称每个人在自己文化环境里愿意做，但「你做不成，你的文化是不允许这种现象生存的」；当年明月坦言很不愿意，因为很多时候像盲从。
+- **对死亡的看法**：当年明月称日本人看樱花只看落的那天，因岛国生态环境恶劣，对死亡不是藐视而是有点向往、不惧怕，甚至藐视生命；他认为二战日军在华暴行与此有关。
+- **马先生的反驳**：马先生不认同「藐视生命」的说法，认为日本民族不是藐视生命而是「重视」，是翻过来的；经济危机时日本很多身家万贯的人选择自杀。
 ## 明朝历史与《明朝那些事》
-- **写明史原因**：当年明月回应为何写明朝历史：明史资料最多，所以最熟；历史界研究有两个难点，一是先秦（如孙武事迹在《史记》仅一两篇，多为编造），二是明清。
-- **明史资料矛盾**：当年明月指出明史资料堆得比山高（明实录几千万字、明通鉴、明史记事本末、明会典等），但一个事件可能有七个不同说法，如同罗生门。
-- **明朝跌宕起伏**：马先生认为明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变、夺门之变，皇上被瓦剌军抓走又回来，完全构成现代版电视剧情节。
-- **推崇朱元璋**：当年明月承认推崇朱元璋，因其从乞丐到皇帝，历史上由最底层人坐上皇位仅此一个；刘邦好歹是村长或乡长，朱元璋是要过饭的人。
-- **朱元璋定制度**：当年明月指出明朝规章制度由朱元璋定下来，基本上没有太大改动，认为此人了不起。
-- **英雄史观**：马先生认为人的因素最大，改变时势一定是出现一个人，自认是英雄史观；当年明月以《亮剑》李云龙为例，说明会打仗的人不用看兵书，靠战场积累经验。
-- **朱元璋被迫起义**：当年明月讲述朱元璋好友汤和让他参加起义军，他在庙里犹豫怕被杀头，后因送信被听到、被人告发，没办法只能去起义。
-- **历史是发生过的**：当年明月强调历史最重要的是明白它是发生过的、是真的；旁观者觉得一跺脚就去起义好玩，但当时是掉脑袋的风险，站在历史原点前后都看不见。
-- **明朝经验体现**：马先生认为明朝经验有体现，如仁宣盛世，但时间太短不怎么提；晚明尽管史书说政治黑暗、皇帝不上朝，但老百姓生活很好。
-- **晚明市民生活**：当年明月指出明末很多真相被掩盖，市民生活特别轻松，想去哪去哪，皇册都不用了；江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍等市民小说出现是温饱思淫欲的娱乐产品。
-- **明末起义原因**：当年明月指出李自成起义是因为陕西一带发生大规模灾荒，与江南富裕形成对比。
-- **明末工艺与艺术**：马先生指出明末工艺品变得非常精细，日本派大量工匠来交流学习；吴门画派文征明、唐寅等能画出小桥流水，因生活好心态轻松；到八大山人朱耷时画翻白眼，因对社会愤愤不平。
-- **历史教训**：当年明月引用“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，认为历史事件发生时有背景，你不比前人聪明甚至可能更笨，当时情况出现你也得这么办。
-- **史书是照片**：当年明月比喻史书记载下来的是照片，而古人的生活是录像；你不知道那一幕之前和之后是什么，所以不能套用经验教训，一定要代入。
-- **明朝有趣之处**：当年明月认为明朝什么都有——宦官专政（魏忠贤）、文官专政（张居正）、皇帝专政（朱元璋），皇帝出去了还能回来、回来了还能做皇帝。
-- **吴三桂入关**：当年明月指出吴三桂与满清合作入关，除陈圆圆外还有个原因：他认为崇祯死了，入关是为崇祯皇帝复仇；崇祯本可早点跑但不跑。
-- **北京瘟疫**：当年明月提到1644年明朝灭亡那年，李自成打到京城无人抵抗，因有史料记载北京发生瘟疫“疙瘩瘟”（很可能就是天花）；他曾与老师交流认为明朝亡得蹊跷。
-- **王朝三百年大限**：马先生认为中国历史王朝300年是大限，逼近300年自己就没了，和人到八九十岁大限将至一样；严格讲超过300年的只有宋朝，因退让大半个国土保证延续，汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
-- **公司寿命对比**：当年明月以公司作比，世界上公司超过279年的没有几家，而明朝管理几千万人的大摊子。
+- **写明史的原因**：当年明月称别人为什么看明史他不知道，自己写是因为「明史我最熟」，因为明史资料最多。
+- **历史研究两大难点**：当年明月指出历史研究有两个难点——先秦和明清；先秦因《史记》等史料少、事迹多为编造，明清则因资料太多，一个事件可能有七个不同说法，如「罗生门」。
+- **明朝跌宕起伏**：马先生称明朝260多年过程本身就跌宕起伏，几次要死没死，有土木堡之变、夺门之变等各种「之变」；皇上被瓦剌军抓起来、把弟弟扶起来，完全构成现代版电视剧的离奇情节。
+- **推崇朱元璋**：当年明月承认推崇朱元璋，因为他是历史上由最底层的人当皇帝的唯一例子——乞丐出身，刘邦好歹是村长或乡长；要过饭的人当上皇帝，每一层的猫腻全知道，因此疑心重。
+- **朱元璋的制度贡献**：当年明月称朱元璋从一起干到最后推翻元朝、当上皇帝，明朝规章制度由他定下来，基本没有太大改动，是「多了不起的人才」。
+- **英雄史观**：马先生认为「人的因素最大」，改变时势一定是出现一个人，是英雄史观；当年明月以《亮剑》李云龙为例，称会打仗的人不用看兵书，是战场上死死生生积累的经验。
+- **朱元璋起义的逼上梁山**：当年明月讲述朱元璋原在庙里犹豫是否参加起义军，因信差送信被人听到告发，没办法只能去起义；他强调历史最重要的是明白「这事是真的」，旁观者觉得好玩，但当事人是掉脑袋的风险。
+- **经验与兴亡**：窦文涛问中国历史经验是否体现在明朝兴亡上，马先生认为能体现——明朝有仁宣盛世（因时间太短现在不怎么提），晚明虽史书说政治黑暗、皇帝不上朝，但老百姓生活很好。
+- **晚明市民生活**：当年明月称明末很多真相被掩盖，市民生活特别轻松，想去哪去哪、连皇册都不用了；江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍这类市民小说是娱乐产品，说明有养活自己的资本。
+- **明末工艺品与画派**：马先生称明末工艺品彻底改观、变得非常精细，有点像日本工艺，日本派大量工匠来交流；吴门画派文徵明、唐寅都是中后期人物，生活不好画不出小桥流水，到八大山人朱耷画的都是翻白眼，是对社会愤愤不平。
+- **历史教训不可套用**：当年明月引用「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，称史书记载下来的是「照片」，而古人的生活是「录像」，不知道那一幕之前和之后是什么，所以不能套用历史经验。
+- **明朝的「有趣」**：当年明月称明朝什么都有——宦官专政（魏忠贤）、文官专政（张居正）、皇帝专政（朱元璋），皇帝出去了还能回来、回来了还能做皇帝。
+- **吴三桂入关**：当年明月称吴三桂与满清合作入关，除陈圆圆外还有个原因——他认为崇祯死了，当时说法是「我们入关是为崇祯皇帝复仇」，吴三桂很忠诚于崇祯。
+- **1644年北京瘟疫**：当年明月称1644年明朝灭亡那年北京有瘟疫「疙瘩瘟」（可能为天花），李自成打到京城无人抵抗与此有关；他曾与老师交流，认为明朝亡得蹊跷、什么坏事都赶上了。
+- **王朝300年大限**：马先生称中国历史王朝300年是大限，逼近300年自己就没了，和人到八九十岁大限快到了一样；严格讲超过300年大限的只有宋朝（南北宋接上，退让大半个国土），汉朝中间隔断14年、唐朝明朝清朝都没超过。
+- **正德皇帝被写坏**：当年明月称正德皇帝（明武宗）被写坏，因接班的嘉靖是他堂兄弟而非儿子，明武宗实录是嘉靖指派杨廷和等人编的，有偏颇；正德从江南回来在通州先停半年、派人打探京城有无埋伏，说明他「绝不是史料上所写的那么蠢」、非常有城府。
+- **正德皇帝轶事**：当年明月讲述正德要去江南，大臣跪在金水桥前抗议，他气得让锦衣卫打、打死十几个；到扬州要东西没有、有也不给，他让人准备酒席又说吃不了，把酒席折合的银两带回去，「皇帝打秋风」。
+- **天启皇帝当木匠**：马先生称天启皇帝爱当木匠，干完活拆大盆去卖，卖完还打听卖得怎么样，听说卖得很好成就感特大；这从侧面反映当时社会对家具的重视。
 ## 明式家具与审美
-- **审美差异**：马先生解释宋明是典型汉人政权、文人政权，文人审美较高，对美的判断不是表象的；满族是异族，进来后对美的判断都是表象的。
-- **审美变迁**：马先生指出今天凡是外在直观能看到的都卖得非常贵，但100年前晚清到民国初年，值钱的一定是素雅的。
-- **天启皇帝做木匠**：马先生讲述天启皇帝爱当木匠，干完活拆大盆去卖，卖完还打听卖得怎么样，听说卖得很好成就感特大；这从侧面反映当时社会时尚，家具在每个人心里地位高。
-- **明式家具地位**：马先生认为明式家具在国际上地位高绝非偶然，皇帝能下那么大力气去做，可见影响之深；所有偶然中一定有个必然因素。
-- **正德皇帝翻案**：当年明月认为正德皇帝被写坏，因接班的嘉靖是其堂兄弟而非儿子，明武宗实录由嘉靖指派杨廷和等人编修，有偏颇；正德从江南回来在通州先停半年，派人打探京城有无埋伏，说明其有城府。
-- **正德皇帝无后**：马先生指出正德是明朝最荒淫的皇帝（清朝最荒淫的是咸丰），但咸丰留了种，正德没少找女人却不留种，没有正宗传下来，到嘉靖拐了弯。
-- **正德出宫**：马先生认为正德对宫内女人没兴趣，因女人被训练过、禁忌多太保守；出宫找民女，民女不知他是皇帝，家花不如野花香。
-- **正德下江南受阻**：当年明月讲述明武宗要去江南，大臣跪金水桥前抗议，皇帝气坏到锦衣卫打死了十几个人；到扬州要东西没有，有也不给，皇帝只好回去，还让人准备酒席折合银两带回去。
+- **故宫审美的来源**：窦文涛提到一种观点认为故宫大红大紫是满族人的趣味，明朝不是这样；马先生认同，称宋明是典型的汉人政权、文人政权，文人审美较高，对美的判断不是表象的，而满族是异族，对美的判断是表象的。
+- **审美变迁**：马先生称今天凡是外在直观能看到的都卖得贵，但100年前晚清到民国初年，值钱的一定是素雅的，这也是一个发展的过程。
+- **明式家具地位**：马先生称明式家具在国际上地位高绝非偶然，「所有的偶然中一定有个必然的因素」，皇帝能下那么大力气做木匠，可见家具对当时社会影响之深。
 # 关键引语与金句
-&gt; 日本战后以后呢，他用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然，不是偶然的，就是他全民族的这种极端精神，是一个国家在战后这样一个不利的局面下，只需要30年的时间，他进入世界第二经济强国，是以绝对量，不是人均量，绝对量，他是一个世界上这个强国里唯一没有资源的国家。
-&gt; 中国的文化精神是中庸……讲究这个世界上有一种道啊，不是对也不是错，不是黑也不是白啊，不是真理。也不是谬误，就是太极。但是这条路可以走得通，叫融合。
-&gt; 日本的精神就恰恰相反，他坚持一个原则……当他忘记所有的事情，只记得把这一炮开出去，他就达到了他的最高境界。
+&gt; 慢慢来才是最快的方法。
+背景：当年明月在讨论日本文化中人人各司其职、不耍小聪明时，引述别人讲过的一句话，用以说明专注本分反而最有效率。
 &gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-&gt; 历史。他那个事儿发生的时候是有背景的……当你要明白你不比前人聪明，你甚对你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办，甚至还不如前人。
-&gt; 我们史书上记载下来是什么？照片……而我们实际上我们的生活古人的生活都是录像，就咱们都是活了这么多年，一直往这往下面走，但是在史书上下来的只是一个照片咔嚓，但你不知道为那一幕之前和之后是什么。
-&gt; 慢慢来才是最快的方法。
-&gt; 一个人到战场上死死生生多少年啊，没写没没死，最后积累下来经验啊。然后我一上战场我就知道，唉敌人会往哪走，我该怎么打。</t>
+背景：当年明月回应窦文涛关于明朝兴亡经验教训的提问，强调历史事件有其特定背景，不能简单套用前人经验。
+&gt; 你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。
+背景：当年明月解释为何后人常觉得前人决策愚蠢——因为后人站在事后视角，而当事人身处其中无法预知结果。
+&gt; 所有的偶然中一定有个必然的因素。
+背景：马先生回应天启皇帝痴迷木工一事，说明明式家具在国际上地位高绝非偶然，反映当时社会对家具的重视。
+&gt; 一个人到战场上死死生生多少年啊，没死，最后积累下来经验。然后我一上战场我就知道，唉敌人会往哪走，我该怎么打。
+背景：当年明月以《亮剑》中李云龙为例，说明朱元璋这类人靠实战经验而非书本知识取得成功。
+&gt; 日本是终身雇用了，人家还是基金特别高。
+背景：当年明月回应西方经济学无法理解日本终身雇佣制下仍保持高效率的现象，指出日本打破了经济学常规预期。
+&gt; 他因为知道每一层的猫腻，他就疑心重，这是肯定的，但他全知道，这种人才上。
+背景：马先生评价朱元璋——因要过饭、从最底层爬上皇位，深知各级官员的猫腻，因此疑心重，但也因此能驾驭群臣。</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>84.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17496/4937</t>
+          <t>17496/4748</t>
         </is>
       </c>
     </row>
@@ -13680,68 +13556,77 @@
       <c r="C37" t="inlineStr">
         <is>
           <t># 访谈概述
-余华在访谈中回顾了其文学创作历程与人生感悟。作为当代著名作家，余华的代表作包括《活着》《兄弟》《第七天》《文城》等。本次采访围绕其创作阶段划分、写作状态、对批评的态度、网络热度下的公众人物身份、中年危机与自我调节，以及未来写作计划等议题展开。
-余华将文学创作分为三个阶段：逼自己坐下来写、卡夫卡的启发、威廉·福克纳的视觉描写方法，并认为3.0版本后写作已畅通无阻。他坦言最好的写作状态在40多岁到50岁，但那段时光被浪费，只出了两部作品；2006年开始的一部长篇小说因感觉远去而未完成，计划在2029年前完成下一部长篇。余华希望以遗忘的姿态留在历史长河，不再追求高度而追求宽度，并打算先写完一个喜剧改变读者印象。
-关键锚点包括：作品《兄弟》（1996年动笔、2004年重写）、《第七天》《文城》；童年被海流带到40里外的经历；三亚的童年星空。访谈看点在于余华独家披露了与苏童、莫言同游莎士比亚故居的细节，直言莫言在雕塑前发誓成为剧作家是“瞎扯”，并指出网上关于他的话有一半不是他说的。
+本次访谈中，作家余华（代表作《活着》《兄弟》《第七天》《文城》）接受采访，回顾其写作历程与文学理念，并回应外界批评与网络时代的热度。访谈主线围绕余华将文学创作分为1.0（逼自己坐下来写）、2.0（受卡夫卡启发、遭遇心理表现障碍）、3.0（受威廉·福克纳影响、以视觉描写呈现心理）三个阶段展开，覆盖写作状态与时间浪费、作品间隔与未来计划、童年游泳经历与人生感悟、对仁慈的看法与喜剧计划、对高度与宽度的追求、对批评的态度、网络时代与公众人物、中年危机与自我调节、历史长河中的姿态等议题。余华核心观点包括：3.0版本后写作已畅通无阻，不再升级；现在不再追求高度、转而追求宽度；希望以遗忘的姿态留在历史长河中。关键锚点包括《兄弟》出版于2006年（1996年动笔、2004年重写）、《第七天》与《文城》间隔八年、长篇间隔十年/八年/八年。访谈看点在于余华亲述2006年未完成长篇的遗憾、与莫言苏童同游莎士比亚故居的细节，以及他澄清互联网上关于自己的话有一半并非本人所说。
 # 访谈详细记录
-## 文学创作历程与阶段
-- **创作三阶段**：余华将文学创作分为三个重要时刻——逼自己坐下来写、卡夫卡的启发、威廉·福克纳的视觉描写方法。他认为3.0版本后写作已畅通无阻，不再升级。
-- **写作起点**：余华强调「坐下来让屁股和椅子建立友谊」是年轻时候最重要的事；若没有躺在床上幻想作品成功，可能就不会去写。
-- **早期目标**：余华年轻时目标是对着托尔斯泰和陀思妥耶夫斯基，现在知道距离不可逾越，但那种野心支撑他一篇篇写下来。
-- **卡夫卡启发**：余华认为写作越写越难，会遇到对心理表现的障碍；卡夫卡给了他重要启发。
-- **福克纳方法**：余华提到威廉·福克纳写穷白人杀富白人的内心状态，采用「让心脏停止跳动，让眼睛睁开」的方式——心理描写没有心理，是视觉描写。
-- **《狂人日记》例证**：余华举例「赵家的狗看了我一眼」，认为通过视觉描写能精确表达精神状态；他去过精神病医院，精神病人说话逻辑清晰，只是方向不同。
-- **3.0版本成熟**：余华认为3.0版本后写作畅通无阻，《活着》可能被认为是4.0版，但对他来说已不是难题——写农民要用最朴素的语言。
-## 写作状态与作品创作
-- **最佳状态被浪费**：余华认为最好的写作状态在40多岁到50岁，但那段时光被浪费，只出了两部作品，现在非常可惜。
-- **未完成长篇**：余华2006年开始写一部长篇小说，实践跨度与《兄弟》相同，但从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写；现在身体状态能维持激烈，但那个时代的感觉没了。
-- **写作时间预估**：余华表示能好好写作的时间可能只剩十年左右，在三亚的工作就是写作、读书听音乐和锻炼。
-- **下一步计划**：余华希望尽快完成下一部长篇，计划在2029年前；开学时要与学生见面，处理学校事务后回三亚继续写作。
-- **《十八岁》写作**：余华提到《十八岁》一天就写完6000字，对他这种写字慢的人是奇迹。
-## 对批评的态度与自我调节
-- **《兄弟》遭遇**：余华出版《兄弟》时认为肯定是一片赞扬，结果一片骂声，让他有点糊涂；当时接受了很多采访努力解释作品。
-- **《第七天》应对**：余华出版《第七天》时只接受了一个采访，告诉朋友们做好被骂的准备，结果果然一片骂声。
-- **《文城》情况**：余华出版《文城》时提醒朋友骂声可能又来，但骂声少了一点，骂人的人也累了。
-- **对待批评方式**：余华找到对待批评的方式——第一不要去看，第二有些批评要重视。
-- **宋凡平批评回应**：余华认为批评宋凡平太完美没有道理，因为宋凡平是阶段性人物，只能写他在这个阶段的表现。
-- **《第七天》批评接受**：余华接受「社会底层人未必都善良」的批评，认为这句话说得很好，会在以后写小人物时考虑——他们在现实中会勾心斗角，但不会置对方于死地。
-## 网络热度与公众人物身份
-- **冷静期**：余华曾停一年所有活动和采访，处于冷静期；当时拒绝了一个活动邀请，说「我现在在一年的冷静期中间」。
-- **自媒体时代**：余华发现自媒体时代会把几十年前的事情翻出来，以前说过的话都翻出来；网上关于他的话有一半不是他说的。
-- **不担心热度消散**：余华不担心喜欢会消散，因为他的工作不是说话，是写作，不说话也挺好。
-- **网络走红不可控**：余华认为一个人在互联网上火起来不是自己能掌握的，可能因一句话突然被关注，也可能因一句话引发愤怒。
+## 写作阶段与文学理念
+- **1.0阶段**：余华认为写作第一步是逼自己坐下来写，让屁股和椅子建立友谊；若没有离开书桌躺到床上时幻想作品成功，可能就不会去写。
+- **2.0阶段**：受卡夫卡启发，写作越写越难，遇到心理表现的障碍；余华认为写内心平静的人物没有意思，内心动荡的人物才值得写。
+- **3.0阶段**：受威廉·福克纳影响，采用视觉描写手法——「让心脏停止跳动，让眼睛睁开」，心理描写没有心理，通过视觉精确表达人物状态。
+- **3.0后畅通无阻**：余华认为3.0版本后写作已畅通无阻，不再升级；《活着》可能被视为4.0版，但对他已不是难题，因为写作已成熟。
+- **语言与人物匹配**：受访者认为写一个没文化的农民讲述自己故事，必须用最朴素的语言，不能用华丽语言，因为那不是人物的本色。
+## 写作状态与时间浪费
+- **最佳状态错失**：余华认为最好的写作状态在40多岁到50岁，但那时玩掉了，只出了两部作品，现在非常后悔。
+- **未完成长篇**：2006年开始写一部长篇小说，时间跨度与《兄弟》相同，但从个人角度而非时代角度出发，想用接近陀思妥耶夫斯基的激烈方式写，现在身体状态还能维持激烈，但感觉没了。
+- **感觉远去**：受访者表示80年代和90年代的感觉都在远去，很难找回来；他估计自己能够好好写作的时间可能还有十年左右。
+- **当前工作安排**：余华在三亚的工作很简单——写作、读书听音乐、锻炼。
+## 作品间隔与未来计划
+- **长篇间隔**：主持人梳理余华长篇间隔——《在细雨中呼喊》到《兄弟》隔了十年，《兄弟》到《第七天》隔了八年，《第七天》到《文城》又隔了八年。
+- **下一步计划**：余华希望下一步作品快一点，已把这边整理完，开学时与学生见面、处理学校事务后回三亚继续写作，安安静静把感觉找回来。
+## 童年游泳经历与人生感悟
+- **海流经历**：余华童年每年夏天在海盐游泳，有一次进入海流，知道不能挣扎只能跟着走，一直到了40里外的地方才爬上来，赤脚沿海边走回来，天快亮了。
+- **人生即宽广**：受访者认为第一次看到大海时感受到的宽阔就是人生；小时候的人生感受是向前看的，现在的人生感受是往后看的，回忆占多了。
+- **海流中的心态变化**：余华在海流中从紧张害怕到放心，因为了解杭州湾海域，知道海流只会把他带回海岸线；看到天空光亮变化时感动了，觉得海浪带他回家了。
+- **三亚星空**：余华在三亚看到童年的星空，因为那里没有污染；晚上常和太太走路看天空，通过光晕发现月光是金色的，不是银色的。
+## 对仁慈的看法与喜剧计划
+- **回应「仁慈」评价**：主持人提到《第七天》出来时有人说余华变得仁慈了，余华回应「我活着也蛮仁慈的」。
+- **喜剧计划**：余华表示自己的作品几乎都是悲剧，这次回来选择了一篇一篇喜剧，想先把一个喜剧写完，改变读者对他的印象——「把悲伤留给虚构，把欢乐留给现实」。
+## 对高度与宽度的追求
+- **从高度转向宽度**：余华表示现在对高度已经不追求了，追求宽度；作为作家，写作能走到的高度就是现在的高度，允许自己下滑但不要太多。
+- **对潜力的认知**：受访者认为年纪大了以后知道自己的能力在哪里、长处在哪里、还有多少潜力；运气来了也许最后一部作品能创新高度，但已不去想。
+- **莫言在莎士比亚故居**：余华说与苏童、莫言三人一起去莎士比亚故居，莫言在雕塑前说要成为剧作家是瞎扯；莫言20多年前就开始写话剧，只是没拿出来。
+- **帽子轶事**：余华在莎士比亚故居买了三顶黑蓝色帽子，上面有莎士比亚名字，三人天天戴着去牛津，但帽子已找不到了；受访者认为莎士比亚没有给予他们任何灵感。
+## 对批评的态度与处理方式
+- **《兄弟》遭遇批评**：余华认为《兄弟》出版时肯定是一片赞扬，结果一片骂声；当时接受了很多采访努力解释作品，但互联网让批评形成浪涛。
+- **《第七天》与《文城》**：《第七天》出来时余华只接受了一个采访，什么都不做，「让他们去骂吧」；《文城》出来时骂声少一点，因为骂人的人也累了。
+- **对待批评两原则**：第一，不要去看；第二，有些批评要重视——没有道理的批评不用理会。
+- **宋凡平批评无道理**：受访者认为批评宋凡平写得太完美没有道理，因为宋凡平是阶段性人物，只能写他在这个阶段的表现，没有人物是完美的。
+- **《第七天》批评有启发**：有人指出社会底层人未必都那么善良，余华认为这句话说得很好；《第七天》是特殊情况，必须把善良在死无葬身之地表现出来，但现实中小人物会勾心斗角，这种分寸会在以后作品中考虑。
+## 网络时代与公众人物
+- **虚假言论**：余华表示互联网上关于他说的话有一半不是他说的，如「想要命好的」「精神内耗」等都不是他说的。
+- **冷静期**：余华曾停了一年，不做任何活动和采访；按过去经验一年就会在媒体上消失，但自媒体时代会把几十年前的事情翻出来。
+- **不担心热度消散**：受访者表示不担心喜欢会消散，因为他的工作不是说话而是写作，不说话也挺好。
 ## 中年危机与自我调节
-- **34岁年终总结**：余华34岁时在年终总结发现成年人的虚无——一年到头，本来对生活充满信心的人变成一个厌世者。
-- **中年危机感受**：余华认为中年危机是所有人都遇到的，现实世界每天重复，只有写作能带来新的东西。
-- **自我调节方法**：余华建议通过选择让自己知道什么、不知道什么来调节不安；如果网上负面消息太多，可以屏蔽不看。
-- **选择权利**：余华认为我们有权利也有能力选择信息，可以选择积极的，哪怕知道可能不是真的。
-## 人生感悟与未来计划
-- **遗忘的姿态**：余华希望以遗忘的姿态留在历史长河，那些能勉强被微风吹进耳朵的人也是勉强吹进来的。
-- **童年游泳经历**：余华小时候每年夏天在海盐游泳，有一天进入海流，知道不能挣扎只能跟着走，被带到40里外的平湖乍浦，赤脚沿海边走回，天快亮了。
-- **大海感受**：余华童年第一次看到大海时感受到宽阔，认为「宽阔的能力就是人生」；小时候的人生感受是向前看的，现在是往后看的，回忆占多了。
-- **海水颜色认知**：余华小时候课本说海水是蓝色的，但海盐的海水是黄的；在海流中紧张害怕，后来放心，因为知道杭州湾的海流只会把他带回家。
-- **三亚星空**：余华在三亚看到童年星空，因为没污染；晚上和太太走路看天空，发现月光是金色的，不是银色的。
-- **喜剧计划**：余华决定先写完一个喜剧，改变读者对他的印象——「把悲伤留给虚构，把欢乐留给现实」。
-- **追求宽度**：余华不再追求高度，追求宽度；认为写作能走到的高度就是现在的高度，允许自己下滑但不要太多。
-- **马尔克斯影响**：余华认为一代中国作家都被马尔克斯误导，都想在一本书里写一个世纪的故事，但没有能力在不到30万字的小说里写出一个世界。
-- **莫言发誓事件**：余华与苏童、莫言一起去莎士比亚故居，莫言在雕塑前发誓要成为剧作家；余华认为那是瞎扯，莫言20多年前就开始写话剧，只是没拿出来。
-- **帽子轶事**：余华在莎士比亚故居买了三顶黑蓝色帽子，上面有莎士比亚名字，和苏童、莫言一模一样；在伦敦和牛津天天戴，但莎士比亚没给予任何灵感，现在帽子找不到了。
+- **34岁的虚无感**：余华34岁时在年终总结中说一个成年人每到年底都会发现一种虚无，一年到头本来对生活充满信心的人变成一个厌世者。
+- **中年危机的本质**：受访者认为中年危机是突然发现没有那么多新的东西，只有写作能得到一些新的东西，虚构的世界带来新东西，现实世界每天重复。
+- **自我调节方法**：余华认为发生的事情无法选择，但可以选择让自己知道什么、不知道什么；网上负面消息太多时就不看，屏蔽掉——我们有权利也有能力选择。
+## 历史长河中的姿态
+- **遗忘的姿态**：余华希望以遗忘的姿态留在历史长河中，那些能勉强被微风吹进耳朵的人也是勉强吹进来的。
+- **历史长河的主题**：受访者认为假如历史长河里有一个主题，这个主题就是一个一个世界、一个一个的人。
 # 关键引语与金句
-&gt; 假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的，坐下来让屁股和椅子建立友谊，这是很重要的。
-&gt; 当时我觉得我将可能我的目标是对着那个托尔斯泰和陀思妥耶夫斯基去的，现在我知道我离他们的距离是不可逾越的，但是我就就是这种野心，这种幻想，然后呢能够支撑让我一篇篇写下来。
-&gt; 我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。对吧？然后那个嗯我剩下的我可能我的那个能够好好写作的时间，可能也就是十年左右。
-&gt; 发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。
-&gt; 假如那个历史的长河里边有一个主题的话，这个主题就是。一个一个世界，一个一个的人。
-&gt; 我在这的工作很简单，就就是那个写作，然后呢读书听音乐。还有就是锻炼。
-&gt; 把悲伤悲伤留给虚构，把欢乐留给现实。</t>
+&gt; “我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。”
+&gt; 背景：余华谈及2006年开始写的一部长篇小说未能完成，感慨当年感觉已远去，写作时间可能只剩十年左右。
+&gt; “兄弟出版的时候，我认为肯定是一片赞扬……结果一片骂声弄得我有点糊涂。”
+&gt; 背景：余华回忆《兄弟》出版时带着期待却遭遇猛烈批评，当时还接受大量采访努力解释作品。
+&gt; “坐下来让屁股和椅子建立友谊，这是很重要的。”
+&gt; 背景：余华谈写作1.0阶段，强调逼自己坐下来写是年轻时候最重要的事。
+&gt; “福克纳所采用的方式就是让心脏停止跳动，让眼睛睁开。心理描写没有心理，它是视觉描写。”
+&gt; 背景：余华谈写作3.0阶段受威廉·福克纳启发，用视觉描写呈现人物内心状态。
+&gt; “把悲伤留给虚构，把欢乐留给现实。”
+&gt; 背景：余华回应作品几乎都是悲剧的评价，并计划先写完一部喜剧改变读者印象。
+&gt; “我对高度已经不追求了，我现在追求这个宽度。”
+&gt; 背景：余华谈年纪渐长后不再追求写作高度，转而追求宽度，允许自己下滑但不要太多。
+&gt; “发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。”
+&gt; 背景：余华回应如何面对中年危机与负面消息，提出自我调节的方法是主动屏蔽。
+&gt; “假如那个历史的长河里边有一个主题的话，这个主题就是。一个一个世界，一个一个的人。”
+&gt; 背景：余华回答希望以遗忘的姿态留在历史长河中，引用维吉尔的话作结。</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>63</v>
+        <v>77.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11212/3215</t>
+          <t>11212/3579</t>
         </is>
       </c>
     </row>
@@ -13852,91 +13737,71 @@
       <c r="C38" t="inlineStr">
         <is>
           <t># 讲座概况
-本场讲座由主讲人（原文未提及姓名与机构头衔）围绕**柏林战役**展开，以讲解结合听众问答的形式进行。讲座旨在系统梳理这场二战欧洲战场最后一次大规模战斗的背景、进程与影响，面向对二战历史感兴趣的听众。内容主要覆盖六个板块：**战役背景与双方态势**、**双方兵力与部署**、**战役过程与关键事件**、**英美未攻柏林的原因**、**战役影响与后续**，以及**影视书籍推荐**。
-讲座的核心判断有三：其一，柏林战役是**人类历史上最大规模的城市作战**，苏军以约**250万人**对德军约**100万人**形成合围，从北部什切青到南部德累斯顿展开攻势；其二，苏联从高层到基层团结一致，以占领柏林为目标不惜代价强攻，因为占领柏林意味着在战后获得至高无上的地位；其三，柏林战役奠定了**冷战欧洲部分的基调**，直接导致德国分裂为东西两个德国，直至1990年才重新统一。关键锚点包括：苏军进抵奥德河—尼斯河一线距柏林仅**60公里**、1945年**4月16日**战役打响、**5月2日**柏林德军投降。对听众而言，本讲有助于理解二战收尾阶段苏德双方的军事博弈、盟国间的政治考量，以及战后欧洲格局的形成逻辑。
+本次讲座由主讲人（姓名未提及）以访谈对话形式讲解**柏林战役**，面向对二战历史感兴趣的听众，系统梳理了战役背景、双方兵力部署、进攻过程、关键事件与后续影响，并穿插解答听众关于城市作战、希特勒自杀、英美未攻柏林及影视书籍推荐等疑问。讲座围绕**战役背景与双方态势、兵力与部署、战役过程与关键事件、城市作战特点、英美未攻柏林原因、战役细节趣闻、战役影响与后续、影视书籍推荐**八个板块展开。核心判断包括：柏林战役是**二战欧洲战场最后一次大规模战斗**，也是苏德战争最后一场大规模战役；苏军以**约250万人**对德军**约100万人**形成合围，从什切青到德累斯顿实施包围；战役奠定了**冷战欧洲部分的基调**，直接导致德国分裂为东西两个德国。关键锚点包括：战役自1945年4月16日持续至5月2日，希特勒于4月30日与夫人艾娃·布劳恩在地堡自杀，5月9日德国无条件投降。对听众而言，本讲有助于理解二战终结阶段苏德双方的战略博弈、城市攻坚战的残酷性，以及柏林战役对战后欧洲格局的深远塑造。
 # 核心观点与论证
 ## 论点：柏林战役的战略背景与先机
-- **战役定位**：柏林战役是第二次世界大战欧洲战场的最后一次大规模战斗，也是苏德战争期间苏联和德国进行的最后一场大规模战役，1945年同盟国和苏俄已从不同方向攻入德国本土。
-- **苏军态势**：苏军进抵奥德河、尼斯河一线（今德国和波兰边境地区），距离柏林仅60公里，已获得先发制人的机会。
-- **英美态势**：英美联军才刚到达易北河一带，距离柏林还有100到120公里，落后于苏军。
-- **苏联动机**：柏林是法西斯德国大本营及纳粹最大巢穴，苏联从上到下团结一致，以柏林为目标进行不惜代价的强攻，认为占领柏林可在二战后获得至高无上地位。
-## 论点：双方兵力部署与合围计划
-- **苏军指挥**：白俄罗斯第一方面军指挥官为朱可夫元帅，乌克兰第一方面军指挥官为科涅夫元帅，制定两个方向进攻计划。
-- **北路突击**：白俄罗斯第一方面军从奥德河一线、奥德法兰克福方向北部对柏林进行突击与包围。
-- **南路迂回**：乌克兰第一方面军由克拉科夫及德累斯顿方向前出，从南部绕到柏林前突至波茨坦地区，对柏林实施西部包围。
-- **苏军兵力**：苏军两个方面军总计约250万人，从北部什切青到南部德累斯顿共同形成合围网。
-- **德军构成**：德军防守部队主要为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（民兵，由年纪较大的老人及16岁以下孩子组成），总人数约100万人。
-- **德军防线**：德军防线从柏林到桑多梅日桥头堡及奥德河一带，主力为从波兰、白俄罗斯方向撤退的中央集团军群残兵。
-## 论点：战役第一阶段与推进过程
-- **进攻发起**：1945年4月16日，苏军以数以千计的火炮和卡秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河突击，乌克兰第一方面军越过尼斯河展开突击。
-- **推进受阻**：因德军在桑多梅日桥头堡修筑的防线，苏军直到4月20日左右才进抵柏林城区（今柏林潘科区及帕卡洛镇一带）。
-- **突入市区**：4月24日白俄罗斯第一方面军突进柏林市区，此时科涅夫元帅的乌克兰第一方面军仍在艰难摸索向柏林边缘靠近。
-- **德军抵抗**：德军温克的第十二集团军与苏军一直进行周旋，是战役中表现突出的德军部队。
-## 论点：希特勒之死与柏林陷落
-- **婚礼与自杀**：4月29日希特勒与情妇艾娃·布劳恩举行婚礼，4月30日柏林已被苏军围死、红军距地堡仅两条街，希特勒不甘被俘，夫妇双双饮弹自尽。
-- **尸体处理**：希特勒死后部下用汽油焚烧其尸体，至今未见到遗体全貌，只获得一堆烧焦的焦炭，外界说法不一、缺乏确切证据。
-- **谣言影响**：除少数亲信外，大部分人不相信纳粹覆灭，以自欺欺人方式麻痹自己继续与苏军战斗，导致民间谣言盛起。
-- **占领国会大厦**：4月30日夜间苏军占领柏林德国国会大厦。
-- **德军投降**：5月2日苏德双方经谈判拉扯后，柏林城防司令魏德林宣布柏林其余所有地区德军向苏军缴械投降，柏林战役结束；少部分第九集团军及温克第十二集团军残部在温克率领下渡过易北河向英美盟军投降。
-- **德国投降**：5月9日德国宣布无条件投降，将其所属领空、领海、机械设备及仍控制的海外属地（荷兰、丹麦、挪威、波罗的海三国地区、捷克斯洛伐克）无条件交与英美盟军及苏俄最高统帅，二战欧洲部分正式结束。
-## 论点：城市作战的特点与危险
-- **城市作战定义**：城市作战中敌人可能从任何地方攻击，坦克和车辆在街道上易受攻击，敌人可用火箭筒和机枪从建筑物或其他街道攻击，**对进攻方非常困难和危险**。
+- **战略态势**：1945年同盟国与苏俄已从不同方向攻入德国本土，纳粹政权覆灭只是时间问题；苏军进抵奥德河、尼斯河一线（今德波边境），距柏林仅60公里，而英美联军刚到易北河一带，距柏林100–120公里，苏联获得先发制人机会。
+- **苏联动机**：占领柏林被视为获得至高无上荣誉的象征——柏林是法西斯德国大本营及纳粹最大巢穴，谁占领柏林谁就在战后获得至高地位，因此苏联从高层到基层团结一致，不惜代价强攻。
+## 论点：双方兵力与部署
+- **苏军编制**：白俄罗斯第一方面军（指挥官朱可夫元帅）从奥德河一线、奥德法兰克福方向北部对柏林突击与包围；乌克兰第一方面军（指挥官科涅夫元帅）由克拉科夫及德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。
+- **兵力对比**：苏军两个方面军总计约250万人，从北部什切青到南部德累斯顿形成合围网；德军防守部队为中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（民兵，含老人与16岁以下少年），总人数约100万人，防线从柏林延伸至桑多梅日桥头堡及奥德河一带。
+## 论点：战役过程与关键节点
+- **第一阶段（4月16日起）**：苏军以数以千计的火炮和卡秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击；因德军在桑多梅日桥头堡的防线修筑，苏军至4月20日左右才进抵柏林城区（潘科区及帕卡洛镇），24日突进市区。
+- **希特勒之死**：4月29日希特勒与艾娃·布劳恩举行婚礼，4月30日柏林已被苏军围死、红军距其地堡仅两条街，希特勒不甘被俘而饮弹自尽，尸体被部下用汽油焚烧；因遗体仅剩焦炭、无全貌证据，外界说法不一，多数人坚信纳粹未覆灭而继续战斗。
+- **战役结束**：4月30日夜间苏军占领德国国会大厦；5月2日柏林城防司令魏德林宣布德军全部缴械投降（除温克第十二集团军及第九集团军残部渡易北河向英美盟军投降外），柏林战役结束；5月9日德国宣布无条件投降，将荷兰、丹麦、挪威、波罗的海三国地区及捷克斯洛伐克等属地交与盟军，二战欧洲部分正式结束。
+## 论点：城市作战的特点
+- **城市作战定义**：敌人可从任何地方（建筑物、街道）攻击，坦克和车辆在街道上易受攻击，敌人可用火箭筒和机枪从建筑或街道发起袭击，因此城市作战非常困难和危险。
 ## 论点：英美未攻柏林的原因
-- **盟国协议**：盟国事先已在战后德国地盘划分占领上达成协议，柏林战后属于苏联，并会分出一半区域给西方盟国（即后来的西柏林）。
-- **艾森豪威尔判断**：美军统帅艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后仍需把西柏林交出、整个德国东部都是苏联占领区，西方盟军还要撤回去，得不偿失。
-- **替代目标**：盟军更愿占领德国精华地带，如慕尼黑、斯图加特、重镇纽伦堡、汉堡、法兰克福等地。
-- **对日作战考量**：打完德国后盟军还有求于苏联，需要苏联帮助一起与日本作战。
-## 论点：战役细节与标志性事件
-- **易北河会师**：西欧部队和东边苏联部队事先没有交流，在易北河会师只是偶然，双方见到对方部队才知道最后合拢，事先双方高层未达成共识，各打各的。
-- **红旗插国会大厦**：著名的「红旗插上国会大厦」照片中，红旗并非标准苏联制式军旗，而是士兵临时用床单和颜料绘制，但具有非常代表性的意义。
-- **摆拍细节**：插旗士兵手上带着三块从德国老百姓手里抢来的手表，摄影师认为有碍国际观瞻，让士兵重新摆拍、不能明面戴抢来的手表。
-## 论点：战役影响与冷战格局
-- **冷战基调**：柏林战役奠定了冷战欧洲部分的基调，德国后来分裂成东西两个德国，边界大致沿从罗斯托克到南部图林根一线形成。
-- **两德统一**：此后一直到1990年，两个德国才进行统一。
-- **二战彻底结束**：1945年9月2日日本在密苏里号军舰上签署无条件投降书，代表第二次世界大战彻底结束。
+- **盟国协议**：盟国事先已就战后德国地盘划分达成协议，柏林战后属苏联并分出西柏林给西方盟国；丘吉尔虽想抢占柏林，但艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后仍需撤出，得不偿失。
+- **战略取舍**：西方盟军选择占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等德国精华地带，将柏林让给苏联；且打完德国后盟军还有求于苏联共同对日作战。
+## 论点：战役细节与影响
+- **易北河会师**：西欧部队与苏联部队事先没有交流，双方在易北河会师纯属偶然，事先高层未达成共识，实为各打各的。
+- **红旗插国会大厦**：著名的「红旗插上国会大厦」照片中红旗并非标准苏军制式军旗，而是士兵用床单和颜料临时绘制；插旗士兵手上戴着三块从德国老百姓手里抢来的手表，摄影师为顾及国际观瞻要求重新摆拍。
+- **冷战格局**：柏林战役奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直至1990年两个德国才统一；日本于1945年9月2日在密苏里号军舰签署无条件投降书，二战彻底结束。
 # 金句总结
-&gt; “谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。”
-&gt; “柏林也是法西斯德国大本营以及纳粹最大的巢穴。”
-&gt; “与其这样，还不如说是尽可能去占领更多德国的精华地带……柏林就让给苏联吧。”
-&gt; “除了少数亲信以外，大部分人都坚信纳粹没有覆灭，还在就是以自欺欺人的方式麻痹自己和苏军进行的就是不同程度的战斗。”
-&gt; “奠定了冷战欧洲部分的一个基调。”
+&gt; 谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。
+&gt; 背景：讲到苏联从高层到基层团结一致、不惜代价强攻柏林时，点明柏林作为纳粹大本营的政治象征意义。
+&gt; 城市作战非常困难和危险。
+&gt; 背景：回答主持人关于城市作战与野外作战区别的提问，说明敌人可从建筑物或街道任何方向攻击、坦克和车辆在街道上易受攻击。
+&gt; 与其这样，还不如说是尽可能去占领更多德国的精华地带……柏林就让给苏联吧。
+&gt; 背景：解释英美为何不攻柏林时，说明艾森豪威尔认为攻占柏林得不偿失，转而占领慕尼黑、斯图加特、纽伦堡等地区。
+&gt; 大部分人都坚信纳粹没有覆灭，还在就是以自欺欺人的方式麻痹自己和苏军进行的就是不同程度的战斗。
+&gt; 背景：讲到希特勒尸体被焚烧、外界说法不一后，说明纳粹残余势力以自欺欺人的方式继续抵抗。
+&gt; 奠定了冷战欧洲部分的一个基调。
+&gt; 背景：回答柏林战役胜利后世界格局的提问，指出战役直接导致德国分裂为东西两个德国，边界大致沿罗斯托克到图林根。
 # Q&amp;A 环节
-**主持人**：柏林战役是人类历史上最大规模的战役吗？
-**主讲人**：对，是人类历史上最大规模的城市作战。
-**主持人**：城市作战跟野外作战有什么明显区别？
-**主讲人**：城市作战中敌人可能从任何地方攻击你，你的坦克和车辆在街道上很容易成为目标，敌人可以从建筑物或其他街道用火箭筒和机枪攻击你的部队，所以城市作战非常困难和危险。
+**主持人**：城市作战跟野外作战有什么明显区别或定义吗？
+**主讲人**：城市作战中敌人可能从任何地方攻击，坦克和车辆在街道上易受攻击，敌人可从建筑物或其他街道用火箭筒和机枪攻击，非常困难和危险。
 **听众**：是不是这个战役里面希特勒自杀了？
-**主讲人**：是的。1945年4月30日，柏林已被苏军围死，苏联红军离希特勒所在的地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，于是举枪自尽，和他的夫人艾娃·布劳恩一起。
-**听众**：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么引人关注？
-**主讲人**：因为他自尽后，部下用汽油把他的尸体焚烧了，到今天为止没有见到他遗体的全貌，只获得一堆烧焦的焦炭，外界说法不一，没有确切证据证明。实际上他自杀后，除了少数亲信外，大部分人都坚信纳粹没有覆灭，以自欺欺人的方式麻痹自己和苏军继续战斗，所以各种民间说法流传，导致谣言盛行。
-**听众**：想更详细了解这个战役，有什么影视推荐吗？
-**主讲人**：苏联有他拍的《柏林战役》，德国有《帝国的毁灭》。
-**听众**：那他们的细节或倾向有什么不同？
-**主讲人**：德国角度更多是描写希特勒最后生平以及他关于柏林防守上的人事任命；苏联方面更多强调从高层到基层的各方面描写，高层的运筹帷幄以及基层官兵的舍生忘死。
-**听众**：主要进攻柏林的是苏联方面的部队吗？
-**主讲人**：是的，同时半数的还有波兰共产党的部队。
+**主讲人**：是的。1945年4月30日，柏林已被苏军围死，苏联红军距希特勒地堡仅两条街，希特勒不甘被俘，与夫人艾娃·布劳恩一起举枪自尽。
+**听众**：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么受关注？
+**主讲人**：他自尽后部下用汽油焚烧其尸体，至今未见遗体全貌，只获得烧焦的焦炭，外界说法不一。除少数亲信外，大部分人坚信纳粹没有覆灭，以自欺欺人的方式继续战斗，导致谣言流传。
+**听众**：想更详细了解这场战役，有什么影视推荐吗？
+**主讲人**：苏联有《柏林战役》，德国有《帝国的毁灭》。德国角度侧重希特勒最后生平及柏林防守人事任命；苏联角度强调高层运筹帷幄和基层官兵舍生忘死。
+**听众**：主要进攻柏林的是苏联方面的部队？
+**主讲人**：是的，同时还有半数波兰共产党的部队。
 **听众**：那为什么英美不打柏林呢？
-**主讲人**：丘吉尔当时想抢占柏林，但盟国事先已在战后德国地盘划分上达成协议，柏林战后属于苏联，并会分出一半区域给西方盟国（即后来的西柏林）。艾森豪威尔认为美军攻占柏林会增加不必要的伤亡，且占领后还要撤出，得不偿失；不如尽可能占领德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福。而且打完德国后，盟军还有求于苏联共同对日作战。
-**听众**：我知道两个细节趣事：西欧部队和东边的苏联部队事先没有交流，最后在易北河会师只是偶然，双方见到对方部队才知道合拢，事先高层没有达成共识；另外红旗插上国会大厦那个著名照片，红旗其实不是标准苏联制式军旗，是士兵临时用床单和颜料绘制的。
-**主讲人**：还有一点，当时苏军军纪没有太多约束，插旗士兵手上还带着三块从德国老百姓手里抢来的手表，摄影师觉得有碍国际观瞻，让士兵重新摆拍，不能明面上戴在手上。
+**主讲人**：丘吉尔曾想抢占柏林，但盟国事先已达成协议，柏林战后属苏联，并分出西柏林给西方盟国。艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还需撤出，得不偿失；西方盟军选择占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等精华地带，且盟军还有求于苏联共同对日作战。
+**听众**：西欧部队和东边的苏联部队事先没有交流，易北河会师只是偶然？
+**主讲人**：对，双方高层事先没有达成共识，各打各的，见到对方部队才知道合拢。另外红旗插上国会大厦的红旗是士兵用床单和颜料临时绘制的，非标准军旗；插旗士兵手上带着三块从德国老百姓手里抢来的手表，摄影师觉得有碍国际观瞻，要求重新摆拍。
 **听众**：这场战役大概持续了多久？
 **主讲人**：从4月16日开始，一直进行到5月2日。
 **听众**：有什么书可以看的吗？
-**主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记里关于柏林战役后苏俄和西方博弈的内容，涉及西柏林地区划分和德国边境重新划定。
+**主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记中关于柏林战役后苏俄与西方博弈的内容，涉及西柏林地区划分和德国边境重新划定。
 **听众**：柏林战役胜利之后，当时世界形成了怎样的格局？
-**主讲人**：奠定了冷战欧洲部分的基调，德国后来分裂成东西两个德国，边界大致沿从罗斯托克到南部图林根一线，此后一直到1990年两个德国才统一。
-**主持人**：1945年之后日本就投降了，二战也就紧接着结束了？
-**主讲人**：欧洲部分结束了，亚洲部分日本投降后，9月2日在密苏里号军舰上签署无条件投降书，代表第二次世界大战彻底结束。
-**听众**：B站上比较火的鬼畜片段就是这个战役末期发生的？
-**主讲人**：对，那个希特勒鬼畜片段出自电影《帝国的毁灭》，尤其是他大骂温克那一段，指责温克丢下柏林逃跑。</t>
+**主讲人**：奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直到1990年两个德国才统一。
+**主持人**：1945年之后日本紧接着投降了，二战也就结束了？
+**主讲人**：欧洲部分结束了；日本于9月2日在密苏里号军舰上签署无条件投降书，二战彻底结束。
+**听众**：B站上比较火的鬼畜片段就是这场战役末期发生的？
+**主讲人**：对，希特勒鬼畜片段出自电影《帝国的毁灭》，尤其是他大骂温克丢下柏林逃跑那一段。</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>59.7</v>
+        <v>57.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4609/4424</t>
+          <t>4609/3580</t>
         </is>
       </c>
     </row>
@@ -14085,70 +13950,71 @@
       <c r="C39" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为多人参与的开放式讨论，围绕生活中约定俗成规则（结婚、买房、工作）的合理性展开。发言人1认为买房、结婚等规则在经济不好时不合理，发言人2认为必须结婚生子但取决于遇到的人和自身能力，发言人3认为人必须工作是合理的，发言人2补充工作后还需进修学习，发言人1认为工作可能合理但应做自己想做的、不要与钱太保密。
-讨论延伸至理想工作与机器人替代。发言人1理想工作是每天做感兴趣的事，发言人4提出不干活更好，发言人3举例宠物博主工作好，发言人2提到游戏高手。发言人1指出脏活累活没人承担，发言人2提出机器人问世可做苦活累活，发言人3认为应让AI做苦活累活而非创作艺术。发言人2提到蔡明小品中机器人反叛情节，发言人1认为机器人负责生产、人享受挺好但规则能否实现存疑，发言人2担心AI普及后机器人有思维可能革命，发言人1提到上层人保持对平民优势的阶级问题。
-机器人思想意识与风险方面，发言人5提到扫地机器人未来可打扫、做饭，发言人1说养老靠自己。发言人2提出机器人有思想后可能罢工、控制人类，类似终结者；发言人3提到斯皮尔伯格的人工智能电影结局；发言人5认为机器人只需执行命令不必有思想；发言人3认为智能和思想可能无法分开；发言人5担心思想带来不良影响。发言人2提到机器人成为犯罪代理人、职业杀手、超级战士等灾难性后果，并列举单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车等已具备的技术，以及重返德军总部、数码宝贝中的机器人角色。会议最后提及语音分离标注测试，发言人3提到同时两人以上说话会有问题，可以测试；发言人1询问两人一起说话标注情况，标注人需认识声音；发言人1认为单人麦很强；发言人3提议结束会议。
+这是一场由5位发言人参与的开放式脑暴讨论，围绕生活中约定俗成规则的合理性展开，延伸至理想工作、机器人替代与AI风险等话题。讨论覆盖四个板块：约定俗成规则的合理性（结婚、买房、工作）、理想工作与机器人替代、机器人思想意识与风险、语音分离标注测试。讨论以分享为主，未形成明确结论。关键要点包括：发言人1认为买房、结婚等规则在经济不好时不合理，发言人3认为人必须工作是合理的；发言人3提出应让AI做苦活累活而非创作；发言人2担忧机器人有思想后可能反抗人类，后果灾难性；发言人5认为机器人只需执行命令，不必有思想。最后发言人3提议结束，发言人4、发言人2同意，会议结束。
 # 分段速览
 ## 00:00:02-00:01:40 约定俗成规则讨论
-发言人1提出买房、结婚等约定俗成规则不合理，认为经济好时可以、经济不好时不可以；发言人2补充必须结婚生子，但认为取决于遇到的人和自身能力；发言人3认为人必须工作是合理的。发言人2提到工作后还需进修学习、学无止境，发言人1认为工作可能合理，但应做自己想做的、不要与钱太保密。
+发言人1提出买房、结婚等生活中约定俗成的规则其实不合理，发言人2补充必须买房、必须结婚生子，发言人3认为不需要这些规则。发言人1指出经济好时可以，经济不好时不可以；发言人2认为主要取决于遇到什么样的人和自身能力，不能说得太绝对。发言人3提出人必须工作是合理的，发言人2认为工作后还要进修、学无止境，工作之后重新回去学习的情况也说不准。发言人1认为工作可能是合理的，但应该做自己想做的，不要跟钱太保密。
 ## 00:01:40-00:04:13 理想工作与机器人替代
-发言人1理想工作是每天做感兴趣的事，发言人4提出不干活更好，发言人3举例宠物博主每天发宠物视频赚钱，发言人2提到游戏高手。发言人1指出脏活累活没人承担，发言人2提出机器人问世可做苦活累活，发言人3认为应让AI做苦活累活而非创作艺术。发言人2提到蔡明小品中机器人反叛情节，发言人1认为机器人负责生产、人享受挺好但规则能否实现存疑，发言人2担心AI普及后机器人有思维可能革命，发言人1提到上层人保持对平民优势的阶级问题。
+发言人2询问大家理想状态中的工作是什么样的，发言人1表示每天起来想干啥就干啥、按自己兴趣干活很好，发言人4提出有没有可能不干活更好。发言人3举例宠物博主工作特别好，每天发宠物视频剪剪视频就能赚钱，发言人2补充还有游戏高手。发言人1指出总有些脏活累活大家都不想干、没人承担，发言人2提出以后机器人问世，发言人3认为应该让AI去做苦活累活，而不是让它搞创作、艺术。
+发言人2提到蔡明演的小品中机器人被敲了脑袋后开始反叛，把牛皮制品手表皮鞋煮汤的情节，并询问那样人类幸福感是否会更高。发言人1认为机器人负责生产、人负责享受挺好，但这种规则能否实现存疑；发言人2提出AI普及并普惠到实体后，机器人有了自己的思维，只要人类控制得当，以后人类就不用干苦活累活；发言人1提到上层的人不想让平民过得太好，要保持对普通民众的优势，存在阶级问题。
 ## 00:04:13-00:08:05 机器人思想意识与风险
-发言人5提到扫地机器人未来可打扫、做饭，发言人1说养老靠自己。发言人2提出机器人有思想后可能罢工、控制人类，类似终结者；发言人3提到斯皮尔伯格的人工智能电影结局；发言人5认为机器人只需执行命令不必有思想；发言人3认为智能和思想可能无法分开；发言人5担心思想带来不良影响。发言人2提到机器人成为犯罪代理人、职业杀手、超级战士等灾难性后果，并列举单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车等已具备的技术。
-## 00:08:05-00:10:56 游戏动漫机器人角色与语音分离测试
-发言人2提到重返德军总部的超级战士、数码宝贝中的守卫兽、机械装甲兽、安多路兽、机械邪龙兽等机器人角色，并回忆数码宝贝第二部第七集人脸识别剧情。发言人3提到语音分离，同时两人以上说话会有问题，可以测试；发言人1询问两人一起说话标注情况，标注人需认识声音；发言人1认为单人麦很强；发言人3提议结束会议。
+发言人5提到扫地机器人是扫地的，以后发展更好会有能打扫家、做饭的机器人，发言人1说以后养老靠自己。发言人2提出未来机器人有了独立思想意识后开始不受人类控制、搞罢工、反向控制人类，就像终结者里描述的情况，人类成为机器人的奴隶。发言人3提到斯皮尔伯格的人工智能电影也是这个结局，归结到探讨；发言人5认为机器人只要能接受到命令、执行命令就行了，为什么要让它有思想，发言人3认为得有智能但智能和思想可能没法分开，发言人5指出思想可能会带来不好影响。
+发言人2提到机器人成为犯罪代理人、职业杀手、超级战士，独立意识群体罢工后对人类反抗的后果是灾难性的；发言人1提到人把自己改造、给自己安机器，发言人2提到军队用的单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人状态，发言人3说排雷的机械狗和机械车已经在用。
+## 00:08:05-00:10:56 数码宝贝讨论与语音分离测试
+发言人2提到游戏重返德军总部里的超级战士，以及数码宝贝中守卫兽和机械装甲兽进化成安多路兽、有了独立思想意识的情节。发言人4询问守卫兽和安多路兽是哪一部，发言人2说明第一部和第二部都有，并详细讲述第二部最终boss黑暗四天王之一机械邪龙兽是一台精密机械式超级计算机形成生命体，专门为破坏而存在；安多路兽在九几年时通过人脸识别判断出人是谁，第二部第七集主角嘉儿通过记忆和回忆唤醒安多路兽最终记忆。
+发言人3提到语音分离，同时两个人以上说话会有问题，可以测一下；发言人1提到两人一起说话标注怎么样，标注的人得认识声音，发言人5提到身高比较，发言人1说单人麦很强。发言人3提议结束，发言人4、发言人2同意，会议结束。
 # 要点梳理
 ## 生活中约定俗成规则的合理性
 - **发言人1**：买房、结婚等规则不合理，经济好时可以，经济不好时不可以。
-- **发言人2**：必须结婚生子，但取决于遇到的人和自身能力，不能说得太绝对。
-- **发言人3**：人必须工作是合理的。
-- **发言人2**：工作之后还要重新回去学习、进修，学无止境，活到老学到老。
-- **发言人1**：工作可能合理，但应做自己想做的，不要与钱太保密。
+- **发言人2**：补充必须买房、必须结婚生子；认为取决于遇到的人和自身能力，不能太绝对。
+- **发言人3**：认为不需要这些规则；但提出人必须工作是合理的。
+- **发言人2**：工作后还需重新学习、进修，学无止境，活到老学到老。
+- **发言人1**：工作合理，但应做自己想做的，不要与钱太保密。
 ## 理想工作与机器人替代
-- **发言人1**：理想工作是每天起来想干啥就干啥，参考自己兴趣干活。
+- **发言人1**：理想工作是每天起来想干啥就干啥，按自己兴趣干活。
 - **发言人4**：提出有没有可能不干活更好。
-- **发言人3**：宠物博主工作特别好，每天发宠物视频、剪视频就能赚钱。
-- **发言人2**：提到游戏高手也是理想工作类型。
-- **发言人1**：指出总有脏活累活没人愿意承担。
-- **发言人2**：提出以后机器人问世可做苦活累活。
-- **发言人3**：应让AI做苦活累活，而不是搞创作、艺术。
-- **发言人2**：提到蔡明小品中机器人被敲脑袋后反叛，把牛皮制品、手表、皮鞋煮汤。
-- **发言人1**：机器人负责生产、人负责享受挺好，但规则能否实现存疑。
-- **发言人2**：担心AI普及并普惠到实体后，机器人有自己思维，只要人类控制得当，人类或可不用干苦活累活。
-- **发言人1**：上层的人不想让平民过得太好，要保持对普通民众的优势，存在阶级问题。
+- **发言人3**：举例宠物博主工作好，每天发宠物视频、剪视频就能赚钱。
+- **发言人2**：补充游戏高手也是理想工作类型。
+- **发言人1**：指出总有些脏活累活没人想干，无人承担。
+- **发言人2**：提出以后机器人问世可承担苦活累活。
+- **发言人3**：认为应让AI做苦活累活，而不是搞创作、艺术。
+- **发言人2**：提到蔡明小品中机器人被敲脑袋后反叛，把牛皮制品煮汤的情节。
+- **发言人1**：认为机器人负责生产、人负责享受挺好，但该规则能否实现存疑。
+- **发言人2**：认为AI普及并普惠到实体后，机器人有自己思维，人类控制得当则可能实现。
+- **发言人1**：指出上层人不想让平民过得太好，要保持对普通民众的优势，存在阶级问题。
 ## 机器人思想意识与风险
-- **发言人5**：扫地机器人用于扫地，未来会有能打扫家、做饭的机器人。
-- **发言人1**：以后养老靠自己。
-- **发言人2**：提出机器人有思想意识后可能罢工、反向控制人类，类似《终结者》剧情，人类成为机器人奴隶。
-- **发言人3**：提到斯皮尔伯格《人工智能》电影也是类似结局，归结为哲学问题。
-- **发言人5**：机器人只要能接受到命令、执行命令就行，不必有思想。
-- **发言人3**：机器人得有智能，但智能和思想可能没法分开。
-- **发言人5**：思想可能带来不好影响，如让机器人往前走，它去前面打了个人。
-- **发言人2**：机器人可能成为犯罪代理人、职业杀手、超级战士，独立意识群体罢工后反抗人类，后果灾难性。
-- **发言人1**：提到人把自己改造、给自己安机器。
-- **发言人2**：军队单兵装甲外骨骼、智能枪械、智能火箭发射器已具备，未来列装普及后或不需要单兵轻武器。
-- **发言人3**：排雷机械狗和机械车已在用。
-- **发言人2**：列举《重返德军总部》超级战士、《数码宝贝》守卫兽、机械装甲兽、安多路兽、机械邪龙兽等机器人有独立思想的反派角色。
-- **发言人2**：安多路兽在第二部被黑色魔轮控制时，仍能通过人脸识别判断出人是谁，早期就有此类思维构想。
+- **发言人5**：提到扫地机器人用于扫地，未来可发展出在家打扫、做饭的机器人。
+- **发言人1**：认为以后养老靠自己。
+- **发言人2**：提出机器人有独立思想后可能不受控制、搞罢工、反向控制人类，如《终结者》剧情。
+- **发言人3**：提到斯皮尔伯格《人工智能》电影结局也是机器人归结于探讨。
+- **发言人5**：认为机器人只要能接受到命令、执行命令即可，不必有思想。
+- **发言人3**：认为机器人得有智能，但智能和思想可能没法分开。
+- **发言人5**：指出思想可能带来不良影响，如让机器人往前走它却去打人。
+- **发言人2**：提到机器人可能成为犯罪代理人、职业杀手、超级战士，罢工反抗后果灾难性。
+- **发言人1**：提到人改造自己、给自己安机器的情形。
+- **发言人2**：提到军队单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人状态，列装普及后或不需要单兵轻武器。
+- **发言人3**：确认排雷机械狗和机械车已在用。
+- **发言人2**：提到《重返德军总部》超级战士、《数码宝贝》守卫兽和机械装甲兽进化成安多路兽、机械邪龙兽等机器人有思想意识的角色。
+- **发言人2**：提到《数码宝贝》第二部第七集安多路兽被黑色魔轮控制后仍能通过人脸识别判断人，主角嘉儿用记忆唤醒它。
 ## 语音分离标注测试
-- **发言人3**：同时两人以上说话会有语音分离问题，可以测试。
-- **发言人1**：询问两人一起说话标注情况，标注人需认识声音。
-- **发言人1**：单人麦很强，应该是单人的。
-- **发言人3**：提议结束会议，发言人4、发言人2确认结束。
+- **发言人3**：提到语音分离，同时两人以上说话需要测试。
+- **发言人1**：提到两人一起说话时标注，标注人需认识声音。
+- **发言人1**：认为单人的麦很强，应该是单的。
+- **发言人3**：提议结束，发言人4、发言人2同意，会议结束。
 ## 待确认与风险
-- **机器人有思想后是否会不受控制、反抗人类**：发言人2提出类似《终结者》的担忧，发言人3认为属哲学问题，发言人5认为机器人只需执行命令不必有思想，未达成一致。
-- **机器人是否需要有思想**：发言人5认为不必，发言人3认为智能和思想可能无法分开，存在分歧。
-- **机器人负责生产、人享受的规则能否实现**：发言人1认为挺好但存疑，发言人2提出AI普及后机器人有思维可能革命，发言人1提到上层保持对平民优势的阶级问题。
-- **机器人有思想可能带来不良影响**：发言人5担心思想带来不好影响，如机器人执行指令时伤人。
-- **机器人可能成为犯罪代理人、职业杀手等**：发言人2提出机器人有独立意识后罢工、反抗人类，后果灾难性。</t>
+- **机器人有思想后是否会反抗人类**：发言人2提出如《终结者》剧情，机器人有独立思想后不甘被压迫、奋而反抗并奴役人类；发言人3认为机器人会不会把自己当成被压迫对象是哲学问题。
+- **机器人是否需要有思想**：发言人5认为只需执行命令即可，发言人3认为智能和思想无法分开，发言人5指出思想可能带来不良影响。
+- **机器人负责生产、人享受的规则能否实现**：发言人1认为挺好但存疑，发言人2认为人类控制得当则可能实现。
+- **上层人是否会保持对普通民众的优势**：发言人1指出上层人不想让平民过得太好，存在阶级问题。
+- **机器人风险**：可能成为犯罪代理人、职业杀手、超级战士，罢工反抗后果灾难性。</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3931/3215</t>
+          <t>3931/3308</t>
         </is>
       </c>
     </row>
@@ -14243,61 +14109,60 @@
       <c r="C40" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为一场围绕哥斯拉系列电影的脑暴讨论，由发言人1主导梳理剧情，发言人2参与讨论。讨论覆盖了哥斯拉的起源（1954年首部电影，海底生物吸食核废料变异）、日美不同版本的故事线、角色设定（基多拉、摩斯拉、金刚等）以及核废水主题。
-发言人1详细梳理了美国版三部曲剧情：2014年第一部中哥斯拉与人类携手消灭以核废料为食的雾托物种；第二部《怪兽之王》中人类核试验唤醒沉睡怪兽，基多拉降临，哥斯拉被人类误伤后靠核废料复活并击败基多拉；第三部《哥斯拉大战金刚》中人类反派将基多拉残骸制成机械基多拉，最终金刚与哥斯拉联手将其打败，战斗场景发生在香港九龙。日本版剧情更复杂，2016年《新哥斯拉》中哥斯拉吸收核废料不断升级，最终被无人机投放炸弹耗尽能量并以冷冻剂封印。
-讨论延伸至核废水排放的现实影响。发言人2曾留学日本，当时日本开始排放核废水，其购买中国进口的鱼；发言人1认为即使不吃海产品，日常饮水也可能受影响。发言人2指出日本国产产品因民族自信价格昂贵，中国进口产品便宜。发言人1询问核废水对身体的伤害，发言人2表示不清楚，但提到可能引发白血病等病变。
-发言人1提及切尔诺贝利核事故，当地生物畸形但未变强，核反应堆被水泥封存，普里皮亚季和切尔诺贝利成为鬼城，方圆百里无人区，认为日本排放核废水不如切尔诺贝利负责任。还提及使命召唤4游戏中切尔诺贝利关卡，英国SAS特种部队狙杀车臣派军未成功。
+本次讨论由发言人1主导、发言人2参与，围绕哥斯拉系列电影剧情展开梳理，并延伸至核废水排放的现实影响。哥斯拉首部电影诞生于1954年，距今约70多年，日美两国翻拍多个版本；其起源为海底生物吸食核废料后变异，在日本神话中是大自然守护神，因人类破坏生态而攻击人类。讨论覆盖哥斯拉系列剧情梳理、核废水排放现实影响两大板块，前者涉及《哥斯拉怪兽之王》《哥斯拉大战金刚》等作品及基多拉、摩斯拉等角色设定，后者延伸至日本核废水排放、切尔诺贝利事件等话题。以分享为主，未形成明确结论。关键数字包括：哥斯拉系列首部电影诞生于1954年、距今约70多年、2004年日本电影《哥斯拉最后的战斗》有中国演员章子怡出演、切尔诺贝利核事故区域方圆百里成为无人区。
 # 分段速览
-## 00:00:00-00:05:28 哥斯拉系列电影剧情梳理
-发言人1开场后即进入哥斯拉系列电影讨论，从1954年首部哥斯拉电影讲起，介绍哥斯拉起源为海底生物吸食核废料后变异成庞然大物。他说明哥斯拉在日本神话中是大自然守护神，因人类核试验破坏生态而攻击人类，并梳理了《哥斯拉怪兽之王》中反派基多拉为外星三头龙、《哥斯拉大战金刚》中机械基多拉被金刚与哥斯拉联手打败等剧情，战斗场景发生在香港九龙。发言人1还提到日本神话中的摩斯拉是负责给哥斯拉疗伤的蝴蝶，并说明哥斯拉系列因每次未被真正消灭而有不同版本续集。
-## 00:05:28-00:09:18 日美版本剧情对比
-发言人1继续梳理美国版三部曲剧情：2014年第一部中哥斯拉与人类携手消灭以核废料为食的雾托物种；第二部中人类核试验唤醒沉睡怪兽，基多拉降临，哥斯拉被人类误伤后靠核废料复活并击败基多拉；第三部中人类反派将基多拉残骸制成机械基多拉，最终金刚与哥斯拉联手将其打败。他随后介绍日本版剧情更复杂，2016年《新哥斯拉》中哥斯拉吸收核废料不断升级，最终被无人机投放炸弹耗尽能量并以冷冻剂封印。发言人1还提及2004年日本电影《哥斯拉最后的战斗》有中国演员章子怡参演。
-## 00:09:18-00:10:34 哥斯拉与奥特曼关系讨论
-发言人1说明哥斯拉与奥特曼虽最早都由圆谷英二导演，但属于不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星，两者均为正面形象，未直接战斗过。他提到哥斯拉系列中的翼龙拉顿在奥特曼作品中与奥特曼战斗过，并提及有国产版「奥特曼大战哥斯拉」的AI生成话题。
-## 00:10:34-00:12:01 哪吒大战变形金刚话题
-发言人2提及「哪吒大战变形金刚」电影，称似乎已开拍且为中美合拍。发言人1回应等拍出来再看，随后总结哥斯拉系列从1954年至今的演变脉络，并指出只要日本不停止排放核废水，此类题材就不会停。
-## 00:12:01-00:15:17 核废水排放的现实影响
-讨论转向核废水排放的现实影响。发言人2回忆在日本留学期间日本开始排放核废水，当时购买中国进口的鱼；发言人1认为即使不吃海产品，日常饮水也可能受影响。发言人2指出日本国产产品因民族自信价格昂贵，中国进口产品便宜。发言人1询问核废水对身体的伤害，发言人2表示不清楚，但提到可能引发白血病等病变。发言人1提及切尔诺贝利核事故，当地生物畸形但未变强，核反应堆被水泥封存，普里皮亚季和切尔诺贝利成为鬼城，方圆百里无人区，认为日本排放核废水不如切尔诺贝利负责任。发言人1还提及使命召唤4游戏中切尔诺贝利关卡，英国SAS特种部队狙杀车臣派军未成功。
+## 00:00:00-00:09:48 哥斯拉系列电影剧情梳理
+发言人1开场即切入哥斯拉系列电影讨论，从1954年首部哥斯拉电影讲起，梳理其起源为海底生物吸食核废料后变异，以及在日本神话中作为大自然守护神的设定。随后按时间线展开美国版三部曲剧情：2014年《哥斯拉》中哥斯拉与人类联手消灭以核废料为能源的雾托物种；《哥斯拉怪兽之王》中人类核试验唤醒沉睡怪兽、外星三头龙基多拉降临，哥斯拉被人类误伤后靠核废料复活并击败基多拉；
+《哥斯拉大战金刚》中人类反派将基多拉残骸制成机械基多拉，金刚与哥斯拉联手将其击败，战斗地点包括香港九龙。发言人1还提及摩斯拉为哥斯拉疗伤、2004年日本版《哥斯拉最后的战斗》有章子怡出演，以及哥斯拉系列因主角未被真正消灭而不断推出续集。
+## 00:09:48-00:10:51 哥斯拉与奥特曼关系讨论
+发言人1回应奥特曼与哥斯拉能否同框的问题，指出两者虽同出导演圆谷英二，但分属不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星，且均为正面形象，难以直接对战。同时提到翼龙拉顿作为反派形象，在哥斯拉和奥特曼作品中均与正派角色战斗过。发言人2插话提及哪吒大战变形金刚的中美合拍传闻。
+## 00:10:51-00:15:17 核废水排放的现实影响讨论
+发言人1总结哥斯拉系列IP长盛不衰的原因，认为只要日本不停止排放核废水，此类题材就不会终结，并指出日本排放核废水受美国影响、决定权不在日本。发言人2回忆在日本留学期间因核废水排放而购买中国进口鱼类，并提到日本国产产品因民族自信而价格昂贵。发言人1担心核废水影响饮用水安全、过滤成本高，认为核废水可能导致白血病等病变但不会像哥斯拉那样变异成庞然大物。讨论延伸至切尔诺贝利核事故，发言人1指出普里皮亚季和切尔诺贝利已成鬼城、方圆百里无人区，反应堆被水泥封存，并提及使命召唤4游戏中英国SAS特种部队在切尔诺贝利狙杀车臣派军的关卡。
 # 要点梳理
 ## 哥斯拉系列电影剧情梳理
-- **哥斯拉起源**：1954年首部哥斯拉电影诞生，距今约70多年；起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
-- **哥斯拉定位**：在日本神话中是大自然的守护神，攻击人类是因为人类无限制搞核试验、破坏大自然生态。
-- **系列扩展题材**：人类频繁战争和核试验唤醒沉睡生物、招致外星生物入侵地球；也有哥斯拉作为守护神与人类携手打败其他怪兽和外星生物的剧情。
-- **《哥斯拉怪兽之王》**：反派基多拉为外星生物，是三头龙形象的龙头老大角色。
-- **《哥斯拉大战金刚》**：基多拉被哥斯拉打败后，人类反派势力将基多拉仅存的一个脑袋残骸加装机械装甲复合升级为机械基多拉，金刚与哥斯拉不计前嫌联手将其打败；战斗场景发生在香港九龙。
-- **摩斯拉设定**：日本神话中的蝴蝶，负责给哥斯拉疗伤。
-- **哥斯拉正反派形象**：既有作为反派出现的印象，也有作为正面形象出现——基多拉降临地球时哥斯拉与人类携手对抗。
-- **2004年日本电影《哥斯拉最后的战斗》**：有中国演员章子怡参演。
-- **续集逻辑**：哥斯拉每次都没被真正打败、杀死和消灭，重新沉睡后产生不同版本续集。
-- **金刚与哥斯拉冲突起因**：金刚领地是热带雨林，哥斯拉领地是海洋；海洋把热带雨林淹了，双方因地盘起冲突。
-- **美国版2014年第一部**：另外两个物种（蝙蝠类）以核弹、核废料为能源食物，哥斯拉为维护地球安全与人类携手团灭该物种（雾托）。
-- **美国版第二部《怪兽之王》**：人类频繁核武器实验唤醒全世界沉睡怪兽，基多拉降临地球；人类想用水下子母弹和核试验形式让哥斯拉窒息，结果基多拉是外星物种、武器对其无效，哥斯拉差点被溺死；后来人类重新喂核废料、核武器实爆唤醒哥斯拉，让其打败基多拉。
-- **美国版第三部**：反派残余势力把基多拉仅存有意识的头加装机械，金刚挺身而出与哥斯拉联手解决。
-- **日本版剧情差异**：比美国版更复杂；人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因与其他怪兽不同，反杀外星人控制的怪兽、重新解放地球。
-- **2016年日本版《新哥斯拉》**：海里蜥蜴类生物喝核废水后不断壮大，吸收核废料后升级变大；人类各种武器攻击不仅无效反而增强其战斗力和形态；最终以无人机投放炸弹耗尽能量，再用冷冻剂封印。
-- **哥斯拉与奥特曼关系**：最早都是圆谷英二导演，但属不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正面形象，未直接战斗过；翼龙拉顿在哥斯拉和奥特曼作品中都与正派形象战斗过。
-- **系列作品清单**：1954年最早哥斯拉大战人类，另有哥斯拉大战机械哥斯拉、哥斯拉大战基多拉、哥斯拉最后的战斗、新哥斯拉、2014年新版本哥斯拉的复活、哥斯拉怪兽之王、哥斯拉大战金刚。
-- **题材延续原因**：只要日本不停止排放核废水行为，此类题材不会停。
+- **首部电影**：1954年诞生，距今约70多年，日美两国翻拍多个版本。
+- **哥斯拉起源**：海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
+- **角色定位**：哥斯拉在日本神话中是大自然的守护神，攻击人类因人类无限制搞核试验、破坏大自然生态。
+- **《哥斯拉怪兽之王》**：反派基多拉为外星生物，三头龙形象，是外星生物中的龙头老大角色。
+- **《哥斯拉大战金刚》**：基多拉被哥斯拉打败后，人类反派势力将基多拉仅存的一个脑袋残骸加装机械装甲复合升级，制成机械基多拉。
+- **机械基多拉对决**：机械基多拉差点打败哥斯拉，金刚挺身而出，与哥斯拉不计前嫌联手击败机械基多拉。
+- **战斗地点**：香港九龙是《哥斯拉大战金刚》中的战斗地点。
+- **摩斯拉**：日本神话中的蝴蝶，负责给哥斯拉疗伤。
+- **哥斯拉形象**：有作为反派出现的印象，也有作为正面形象出现——当基多拉降临地球时，哥斯拉与人类携手对抗。
+- **《哥斯拉最后的战斗》**：2004年日本拍摄，有中国演员章子怡出演。
+- **续集机制**：哥斯拉每次都没被真正打败和消灭，重新沉睡后推出续集，不同版本续集持续产出。
+- **金刚与哥斯拉冲突**：金刚领地为热带雨林，哥斯拉领地为海洋，海洋淹没雨林后双方因地盘起冲突。
+- **美国版2014年第一部**：两个吸食核废料的蝙蝠变异物种「雾托」以核弹、核废料为能源食物，哥斯拉为维护地球安全与人类携手将其团灭。
+- **美国版第二部**：人类频繁核武器实验唤醒全球沉睡怪兽，基多拉降临地球；人类试图用水下子母弹和核试验方式让哥斯拉窒息，基多拉因是外星物种武器对其无效，差点把哥斯拉溺死在海里。
+- **哥斯拉复活**：人类重新给哥斯拉喂核废料、核武器实爆将其唤醒，让其打败基多拉。
+- **美国版第三部**：反派残余势力将基多拉唯一有意识的头加装机械，金刚挺身而出与哥斯拉联手解决。
+- **日本版剧情**：人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因与其他怪兽不同，反杀外星人控制的怪兽并解放地球。
+- **《新哥斯拉》（2016年日本版）**：海里蜥蜴类生物喝核废水后不断壮大升级，人类各种武器攻击不仅无效反而增强其战斗力，最终以无人机投放炸弹耗尽能量，再用冷冻剂封印。
+- **主题核心**：哥斯拉与人类战斗主要围绕「人类频繁核试验破坏自然、哥斯拉作为大自然守护神进行报复」这一题材。
+- **哥斯拉与奥特曼关系**：最早都是导演圆谷英二的作品，但属不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星，两者均为正面形象，未直接战斗过。
+- **拉顿**：会飞的翼龙/鸟，在哥斯拉和奥特曼不同作品中分别与正派形象战斗过。
 ## 核废水排放的现实影响
-- **日本留学经历**：发言人2在日本留学时日本开始排放核废水，当时吃的鱼都是买国内（中国）进口到日本的。
-- **饮水影响担忧**：发言人1认为即使不吃日本海产品，平时喝水也可能受影响，过滤只能解决瓶盖成本层面的问题。
-- **日本国产价格**：发言人2指出日本有民族自信，产品打上国产标签就非常贵，虽然东西并不怎么样；中国进口的鱼便宜。
-- **核废水健康伤害**：发言人1询问核废水对身体损耗的具体伤害，发言人2表示不清楚；发言人1提到目前没看到变异，但肯定有得各种白血病等病变的。
-- **切尔诺贝利核事故**：当地生物长得奇怪、变畸形但没说变强；核反应堆被水泥盖住封住，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里是无人区。
-- **责任对比**：发言人1认为日本排放核废水不如切尔诺贝利负责任——切尔诺贝利至少拦截了一下，把反应堆直接拿水泥封住了。
-- **游戏相关关卡**：使命召唤4中切尔诺贝利关卡，车臣派军去挖核废料时被英国SAS特种部队主角狙杀，未狙杀成功、打断一条胳膊（双狙人关卡）。
+- **题材延续判断**：发言人1认为只要日本不停止排放核废水，哥斯拉题材永远不会停。
+- **排放责任归属**：发言人1指出日本排放核废水决定权不在自身，受美国影响，「美国人叫他排，他敢不排嘛」。
+- **日本进口政策**：发言人1提到前段时间不让进口日本海产品，现已放开。
+- **在日留学经历**：发言人2提到在日本留学期间，因日本开始排放核废水，所吃鱼类均购买中国进口到日本的鱼，且国内进口的鱼价格便宜。
+- **饮用水担忧**：发言人1担心即使不吃日本海产品，日常饮用水也会受影响，过滤成本高。
+- **日本国产溢价**：发言人2提到日本有「迷之民族自信」，产品打上国产标签就非常贵，但质量不一定好。
+- **健康影响**：发言人1提到核废水可能导致白血病等病变，但不会像哥斯拉那样喝了核废料马上变异成庞然大物。
+- **切尔诺贝利对比**：发言人1指出切尔诺贝利核事故后，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里无人区，反应堆被水泥封住，相比日本「至少拦截了一下，给封存了」。
+- **游戏关联**：发言人1提到使命召唤4中「双狙人」关卡，车臣派军去切尔诺贝利挖核废料，被英国SAS特种部队主角狙杀，打断一条胳膊。
 ## 待确认与风险
-- **核废水健康风险**：喝了核废水对身体的损耗具体有什么伤害，未获明确回答；可能引发白血病等病变，但无确切数据。
-- **生物变异风险**：核废水是否会导致生物变异，目前未见变异案例，但存在不确定性。
-- **饮水安全风险**：即使不吃海产品，日常饮水也可能受核废水排放影响。</t>
+- **核废水健康影响**：发言人1提问「喝了核废水对身体的损耗会有什么样的伤害」，发言人2回应「我不知道，别问我」，未获明确答案。
+- **变异可能性**：发言人1提问「会不会真的变异」，讨论中确认目前未见变异案例，但存在白血病等病变风险。
+- **核废水长期风险**：发言人1指出核废水排放可能导致生物病变和健康风险，切尔诺贝利核事故区域成为无人区，存在长期辐射风险。</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5319/3577</t>
+          <t>5319/3049</t>
         </is>
       </c>
     </row>
@@ -14538,81 +14403,65 @@
       <c r="C41" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议为一场围绕“18岁以前的深刻印象和记忆”的开放式分享讨论，由发言人1发起，发言人2、3、4、5、6共6人参与。讨论由发言人1以“逃课、网吧打游戏、追星、音乐会”等青春经历为引子开场，成员依次分享各自记忆，整体以漫谈发散方式推进，先后涉及逃课经历、流行游戏、小说漫画、追星乐队、游戏暴力与年龄限制、游戏与电影关系等议题。本场以分享观点为主，未形成统一结论。
-- **成员构成**：发言人1、2、3、4、5、6共6人，均为发言人身份，无姓名信息。
-- **讨论由头**：发言人1开场提出“18岁以前有没有什么特别深刻的印象和记忆”，列举逃课、网吧游戏、追星、音乐会等方向，引导成员分享。
-- **议题范围**：逃课经历、流行电脑游戏（穿越火线、反恐精英、求生之路、仙剑、魔兽争霸等）、小说漫画（郭敬明小说、《名侦探柯南》《老夫子》《意林》等）、追星与乐队、游戏暴力内容与年龄限制、游戏与电影先后关系、塔防游戏与使命召唤剧情。
-- **整体倾向**：以分享个人经历和观点为主，未形成统一结论；成员间有游戏偏好差异（如CS与穿越火线之争、游戏鄙视链讨论），但未深入交锋。
-- **关键锚点**：**2008年**穿越火线国服上线；**18岁**为Steam账号注册年龄限制；**2020年新冠疫情**后《求生之路》重新火爆。
-- **推进方式**：由发言人1主导串联，按“青春记忆→流行游戏→射击游戏→游戏剧情→游戏与电影关系”逐块推进，期间穿插成员自由补充与追问，整体呈漫谈发散状态。
+本次会议为一场围绕“18岁以前的深刻印象和记忆”的分享讨论，由发言人1发起，共6位成员（发言人1至发言人6）参与。讨论由发言人1提出逃课、网吧游戏、追星、音乐会等话题作为由头，成员们依次分享了各自青春期的经历与偏好。议题范围涵盖：18岁前的青春记忆分享（逃课、追星、乐队、漫画、小说、杂志）、流行电脑游戏讨论、第一人称射击游戏与暴力内容讨论、游戏与电影关系讨论、塔防游戏与使命召唤讨论。整体以分享观点为主，未形成统一结论，讨论氛围轻松发散。关键锚点包括：**CS1.5/1.6**、**求生之路第二部**、**Steam账号18岁年龄限制**。讨论推进方式为漫谈式，由发言人1引导话题，成员们围绕游戏、漫画、小说等主题自由发散，逐块展开。
 # 发言要点
 ## 18岁前的青春记忆分享
-- **发言人1**：初中走读，每周一下午4点放学后大家聚集游戏厅、网吧，流行穿越火线（CF）、反恐精英online（CS online）、使命召唤、战地、魔兽等游戏；高中因高考压力不敢逃课，转而追星、搞乐队，追求朋克金属音乐。
-- **发言人2**：18岁前没逃过课，大学才逃过一次；觉得郭敬明小说看着难受、扭曲，提到《梦里花落知多少》；当时喜欢看漫画。
-- **发言人3**：认为逃课是正常现象。
-- **发言人4**：补充上大学逃课不算；当时班里流行看柯南。
-- **发言人5**：特别喜欢郭敬明的小说；还提到《萌化三国》等杂志。
-- **发言人1**：补充当时流行看《名侦探柯南》和香港漫画《老夫子》。
-- **发言人2**：提到当时流行《意林》《读者》《故事会》等杂志，觉得《意林》讲得好，现在都反转了。
+- **发言人1**：初中走读，每周一下午四点放学后大家聚集在游戏厅、网吧，流行穿越火线CF、反恐精英online、使命召唤、战地、魔兽等游戏；高中因高考压力不敢逃课，转而追星、搞乐队，追求朋克金属主题音乐。
+- **发言人2**：十八岁前没逃过课，大学后才逃过一次；觉得郭敬明的小说看着难受、扭曲；喜欢看漫画；初中玩魔兽争霸（非魔兽世界）；认为王者荣耀在游戏鄙视链最底端。
+- **发言人3**：逃课是正常现象；经常玩塔防游戏，如植物大战僵尸、Kindle rush，现在也还在玩。
+- **发言人4**：上大学后逃课不算；当时班里流行看柯南；提到电脑游戏摩尔庄园、赛尔号；玩过CS1.5和1.6；提到植物大战僵尸融合版。
+- **发言人5**：特别喜欢郭敬明的小说；提到萌化三国；玩过仙剑四；质疑穿越火线等游戏没有年龄限制、内容暴力，认为同龄人里没怎么玩过这个。
+- **发言人6**：提到Steam图标是个人头上面有个阀门；喜欢僵尸题材；表哥每年过年给放恐怖片。
 ## 流行电脑游戏讨论
-- **发言人4**：提到电脑游戏摩尔庄园、赛尔号。
-- **发言人1**：询问大家对劲舞团的看法，尤其从女生角度；初中时流行CS online。
-- **发言人2**：提到穿越火线、地下城与勇士；初中玩的是魔兽争霸，不是魔兽世界。
-- **发言人1**：单机最流行的是求生之路，联机局域玩；还提到流星蝴蝶剑。
-- **发言人5**：玩过仙剑四，还玩过仙剑或古剑系列。
-- **发言人4**：认为仙剑三最火，还拍了电视剧。
-- **发言人5**：提到英雄联盟、DOTA，询问是否有鄙视链。
-- **发言人2**：认为撸啊撸和DOTA有鄙视链，王者荣耀在鄙视链最底端。
+- **发言人1**：询问大家流行的电脑游戏，提到劲舞团，尤其问女生角度；初中时流行CS online，高中时单机最流行求生之路，联机局域玩。
+- **发言人4**：提到摩尔庄园、赛尔号。
+- **发言人2**：提到穿越火线、地下城与勇士；初中玩魔兽争霸，不是魔兽世界。
+- **发言人5**：玩过仙剑四，还玩过仙辕剑或古剑四，记不清具体是哪个。
+- **发言人2**：认为英雄联盟和DOTA有鄙视链，王者荣耀在鄙视链最底端。
 ## 第一人称射击游戏与暴力内容讨论
-- **发言人1**：玩过CS1.5和1.6，曾写文章骂穿越火线抄袭，被穿越火线平台封禁，后成为CS反恐精英铁杆粉丝；喜欢僵尸模式，被说跳舞姿势像舞体僵尸。
+- **发言人1**：玩过CS1.5和1.6；因在贴吧和QQ空间写文章骂穿越火线抄袭，被穿越火线平台封禁，后成为CS反恐精英铁杆热衷粉，最喜欢僵尸模式；学校舞蹈队说他跳舞姿势像舞体僵尸。
 - **发言人2**：觉得穿越火线现在看起来像像素游戏。
-- **发言人5**：质疑当时游戏没有年龄限制，认为求生之路等游戏特别暴力，小孩不能玩。
-- **发言人1**：解释求生之路第二部血腥暴力，可用东洋刀、电锯、砍刀砍丧尸，血能喷一脸；有年龄限制，未成年人不能注册Steam账号，需18岁以上。
-- **发言人1**：认为求生之路制作团队精准预测美国政府面对大灾难的表现，2020年新冠疫情爆发后美国政府表现与游戏预测一样，疫情后全世界重新玩这个游戏。
-## 求生之路游戏剧情与角色讨论
-- **发言人1**：描述求生之路剧情——美国政府默不作声导致病毒失控，军队以暴力清理方式介入，主角团不相信政府承诺、自己拿起枪自救，游戏名称由此而来；主角团是无症状感染者，病毒类似狂犬病狂暴病毒感染。
-- **发言人2**：提到欧美玩家爱玩打僵尸游戏，模式一上线欧洲年轻人就疯狂在线。
-- **发言人1**：提到生化危机也是病毒泄露、政府反应迟钝，生化三直接用核武器夷平城市；认为电影没有游戏直观。
+- **发言人5**：质疑穿越火线等游戏没有年龄限制、内容暴力，认为同龄人里没怎么玩过这个。
+- **发言人1**：解释求生之路第二部血腥暴力，能用东洋刀、电锯、砍刀砍丧尸群，能把脑袋和四肢砍飞、血喷一脸，因此有年龄限制，未成年人不能注册Steam账号，需18岁以上。
+- **发言人1**：认为求生之路制作团队精准预测美国政府面对大灾难的表现，2020年新冠疫情爆发后美国政府表现与游戏预测一样，疫情后全世界重新玩起这个游戏。
+- **发言人1**：描述求生之路剧情：美国政府一开始对病毒传播默不作声，导致国家失控，军队强力介入以暴力清理方式处理，结果军队也被感染失控，主角团不相信政府承诺、自己拿起枪自救，最后去荒岛开辟新住处。
+- **发言人2**：提到欧美玩家爱玩打僵尸游戏，模式一上线欧洲玩家就疯狂在线，整个欧洲年轻人都在打僵尸。
+- **发言人1**：提到生化危机也是病毒泄露、政府反应迟钝不作为导致失控，生化三直接用核武器把整个城市夷平。
 - **发言人2**：觉得生化危机恐怖，不敢玩。
-- **发言人5**：分享过年和表姐表弟看恐怖片，大家都跑了。
-- **发言人6**：提到表哥每年过年放恐怖片。
-- **发言人1**：提到惊变48小时、死亡鬼屋、生化危机，求生之路是这些作品的综合；在网吧玩求生之路只能玩前一会，没有武器会害怕。
-- **发言人2**：说一切恐惧源于火力不足。
-- **发言人1**：最怕坦克，最烦smoke（长舌头捆人）和jacking（骑肩膀控制主界面）。
-- **发言人6**：提到《最后生还者》游戏挺火。
-- **发言人1**：描述《最后生还者》主角团差点被军队物理消灭，后对军队反杀杀出血路。
+- **发言人5**：提到过年时跟表姐表弟一群人看恐怖片，大家都跑了。
+- **发言人1**：提到惊变48小时、死亡鬼屋、生化危机等作品，求生之路是这些作品的综合；在求生之路里最怕坦克，最烦smoke和jacking——smoke会用长舌头捆人，jacking会骑在肩膀上让人控制不了主界面。
+- **发言人2**：认为一切恐惧源于火力不足。
 ## 游戏与电影关系讨论
-- **发言人2**：询问游戏和电影先后关系。
+- **发言人2**：询问游戏和电影哪个先出，举例生化危机。
 - **发言人1**：回答生化危机是先有游戏后有电影；求生之路是在惊变48小时、生化危机基础上，先有电影后有的游戏。
-- **发言人4**：询问变形金刚先有玩具还是电影。
-- **发言人1**：回答变形金刚先有玩具，后来有MV和电影，提到绿日（green day）乐队；认为变形金刚抄袭日本题材，电影有点翻拍盗版感觉。
+- **发言人4**：提问变形金刚先有的啥。
+- **发言人1**：认为变形金刚先有玩具，后有MV和电影，提到绿日（green day）乐队出了介绍变形金刚的MV。
 - **发言人2**：提到变形金刚玩具能扭吧扭吧变成车。
+- **发言人1**：觉得变形金刚有点抄袭日本题材，电影有点翻拍盗版的感觉。
 ## 塔防游戏与使命召唤讨论
-- **发言人3**：小时候经常玩塔防游戏，如植物大战僵尸、Kindle rush，现在也还在玩。
+- **发言人3**：经常玩塔防游戏，如植物大战僵尸、Kindle rush，现在也还在玩。
 - **发言人4**：提到植物大战僵尸融合版。
-- **发言人2**：提到植物大战僵尸有特别变态的版，后期满屏子弹，电脑都卡扛不住。
-- **发言人1**：询问使命召唤玩得多不多。
-- **发言人2**：认为使命召唤这游戏太男性化。
-- **发言人1**：介绍使命召唤黑色行动是冷战时期美国和苏联结合真实历史的明争暗斗；现代战争第一部贴合车臣战争、伊拉克战争、海湾战争，后期俄罗斯反杀美国本土、吊打北约的设定，结合当前俄罗斯在乌克兰的表现，有点高估俄罗斯。
+- **发言人2**：提到植物大战僵尸有特别变态的版，后期满屏全是子弹，电脑都卡扛不住。
+- **发言人2**：觉得使命召唤这游戏太男性了。
+- **发言人1**：介绍使命召唤黑色行动是冷战时期美国和苏联结合真实历史进行明争暗斗、非官方台面上的军事秘密行动；现代战争第一部贴合车臣战争、伊拉克战争、海湾战争，但后来美国挑衅俄罗斯、俄罗斯反杀到美国本土、吊打北约，结合当前俄罗斯在乌克兰的表现，有点高估俄罗斯了。
 # 共识形成
-- **一致意见**：与会者普遍认同18岁前青春记忆以**网吧游戏、追星、漫画与小说**为核心载体，且多数人承认逃课是常见现象（发言人3称「逃课是正常的现象」，发言人4补充「上大学了就不算了」）。在游戏讨论中，大家一致认为**《求生之路》第二部血腥暴力程度高**，需18岁以上才能注册Steam账号游玩；同时认可该游戏制作团队精准预测了美国政府面对大灾难的表现，2020年新冠疫情后该游戏重新火爆。
-- **倾向性认识**：在游戏鄙视链问题上，发言人5提出英雄联盟、DOTA、王者荣耀之间存在鄙视链，发言人2认为**王者荣耀处于鄙视链最底端**，与会者未提出异议。在游戏与电影先后关系上，发言人1明确**《生化危机》先有游戏后有电影**，《求生之路》先有电影后有的游戏，**变形金刚先有玩具后有MV和电影**，此口径未被反驳。
-- **主要分歧点**：发言人1与发言人2、5在游戏暴力与年龄限制上存在分歧——发言人5质疑「那个游戏没有什么年龄限制，为什么我印象中那是我姑父还有我叔叔他们玩的游戏，特别特别暴力，那小孩能玩吗」，发言人1则解释求生之路第二部有年龄限制、未成年人不能注册Steam账号，但未否认早期游戏缺乏限制的事实。此外，发言人1认为变形金刚「有点抄袭小日本的当时的一些个题材」，发言人2未就此表态，仅提及玩具可变形。
+- **一致意见**：与会者普遍认同18岁前的青春记忆以游戏、漫画、小说、杂志等娱乐活动为主，且**逃课、去网吧打游戏是当时常见的集体行为**。发言人3认为逃课是正常现象，发言人4补充上大学后不算逃课，发言人2表示自己18岁前未逃过课、大学后才逃过一次。
+- **倾向性认识**：在游戏讨论中，多数成员认可**穿越火线、CS、求生之路、魔兽争霸、仙剑系列**等为当时流行游戏；发言人2认为王者荣耀处于游戏鄙视链最底端，发言人5提及英雄联盟、DOTA与王者荣耀之间存在鄙视链，未形成统一排序。
+- **主要分歧点**：发言人1与发言人2、发言人5在游戏暴力与年龄限制问题上看法不一致——发言人1认为求生之路第二部血腥暴力、需18岁以上才能注册Steam账号，且其剧情精准预测了美国政府疫情表现；发言人5质疑此类暴力游戏无年龄限制、同龄人很少玩；发言人2觉得生化危机恐怖不敢玩。此外，发言人1认为变形金刚抄袭日本题材、电影有翻拍盗版感，发言人2仅提及玩具能变形，未就此展开争论。
 # 待探讨问题与后续
-- **未确认**：发言人5质疑《求生之路》等游戏没有年龄限制、内容暴力，未成年人能否游玩；发言人1回应称求生之路第二部有年龄限制，未成年人不能注册Steam账号，需18岁以上，但未进一步核实该限制的实际执行情况。
-- **未定论**：关于《求生之路》中主角团的身份，发言人1解释其是无症状感染者，病毒类似狂犬病狂暴病毒感染，但未与其他成员就此展开深入讨论或达成一致。
-- **未确认**：发言人1认为《求生之路》制作团队精准预测了美国政府面对大灾难的表现，2020年新冠疫情后游戏重新火爆，此观点为个人判断，未获其他成员明确认同或反驳。
-- **未定论**：关于《变形金刚》是否抄袭日本题材，发言人1认为电影有翻拍盗版感觉，但未展开具体依据或引发进一步讨论。
-- **未确认**：发言人1评价《使命召唤：现代战争》后期剧情设定（俄罗斯反杀美国本土、吊打北约）结合当前俄罗斯在乌克兰的表现有点高估俄罗斯，此观点为个人看法，未获其他成员回应。
-- **未提及**：原文未涉及任何后续分工、跟进事项或下次会议约定。</t>
+- **未确认**：发言人5质疑穿越火线、求生之路等游戏没有年龄限制、内容暴力，发言人1解释求生之路第二部有年龄限制、未成年人不能注册Steam账号，但未确认该限制的实际执行情况。
+- **未定论**：关于游戏与电影先后关系，发言人1认为生化危机先有游戏后有电影、求生之路先有电影后游戏，发言人4提出变形金刚，发言人1认为先有玩具后有MV和电影，但未形成一致结论。
+- **未确认**：发言人1认为求生之路制作团队精准预测了美国政府面对大灾难的表现，并称2020年新冠疫情后游戏重新火爆，此判断属个人观点，未获其他成员验证。
+- **未定论**：发言人1认为使命召唤现代战争后期剧情「俄罗斯反杀到美国本土、吊打北约」结合当前俄军在乌克兰表现「有点高估俄罗斯」，发言人6仅回应「感觉都挺歪的」，未展开讨论。
+- **未确认**：发言人2提到植物大战僵尸有「特别变态的版，满屏全是子弹、电脑都卡」，未确认该版本的具体名称或来源。</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>68.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6453/3744</t>
+          <t>6453/3205</t>
         </is>
       </c>
     </row>
@@ -14887,71 +14736,62 @@
       <c r="C42" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论为自由漫谈型，由发言人1发起，围绕古典小说展开，参与者为发言人1至发言人4共4人。讨论由发言人1提议继续《红楼梦》话题开场，随后自然发散至《金瓶梅》《水浒传》《西游记》及东吴二宫之争。议题范围包括：《红楼梦》四大家族与官场暗线、冷香丸制作、《金瓶梅》与《水浒传》的关系、西门庆人物结局、《西游记》中佛教的虚伪、《红楼梦》历史背景及东吴二宫之争。整体以分享观点为主，未形成统一结论。关键锚点：护官符诗句「丰年好大雪，珍珠如土金如铁」、冷香丸需「雨水那一日的雨水、小雪那一日的雪」、如来佛祖收「300两黄金」。讨论按话题逐块推进，由《红楼梦》暗线切入，经《金瓶梅》人物与结局、佛教虚伪，再回到《红楼梦》背景，最后以发言人2提及东吴二宫之争、发言人1提醒时间结束。
+本次讨论为一场围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说情节、人物与历史背景的自由漫谈，由梦婷等四位发言人参与，以分享观点为主，未形成统一结论。讨论由续聊《红楼梦》后四十回引入，随后发散至多部古典名著。议题范围包括：《红楼梦》的四大家族与官场暗线、细节描写与版本差异，《金瓶梅》与《水浒传》的关系及西门庆结局，《西游记》中的佛教虚伪，以及古典小说的历史背景与映射。讨论整体呈漫谈发散式推进，由《红楼梦》官场线切入，经四大家族护官符诗句、冷香丸等细节，自然过渡至《金瓶梅》与《水浒传》的对比，再延伸至《西游记》及东吴二宫之争，各议题间无明确边界。关键锚点包括护官符诗句「丰年好大雪，珍珠如土金如铁」、冷香丸需「雨水日的雨水、小雪日的雪」及四季白花、如来佛祖收「300两黄金」等。
 # 发言要点
-## 《红楼梦》四大家族与官场暗线
-- **发言人3**：提出《红楼梦》有一条官场暗线，四大家族兴衰与朝堂变化相关；王熙凤前期地位高与其兄长在官场地位相关，结局惨因其兄长先死。
-- **发言人4**：质疑四大家族「感觉就没几个人」，每家只知两三人，如王家只登场王熙凤、史家只知史湘云，薛宝钗家也没见什么靠山。
-- **发言人3**：回应薛宝钗家是做生意的，主要是有钱。
-- **发言人1**：背诵护官符诗句——「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」，点出四大家族为贾、史、王、薛。
-- **发言人4**：称护官符说得「都很牛逼，就感觉没什么厉害人家」。
-- **发言人3**：认为四大家族整体都在走下坡路。
-- **发言人1**：认同，称说的就是王朝家族的衰败。
-- **发言人4**：提到小时候看《红楼梦》没看明白，但记得江南吃螃蟹非常讲究，要「又卸钱又卸身」，第一次听说吃螃蟹需要这么多工具。
-- **发言人3**：介绍冷香丸制作需雨水那日的雨水、小雪那日的雪，且要正好碰上每个节气。
-- **发言人1**：补充冷香丸材料为春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
-- **发言人3**：提到薛宝钗嫁给贾宝玉后，贾宝玉不久出家，好多人说他们是无性婚姻；另有版本称薛宝钗后来怀了孩子，但那是狗血版本。
-## 《金瓶梅》与《水浒传》的关系
-- **发言人1**：介绍《金瓶梅》从武松杀西门庆失败后开始写；武松去找西门庆时，西门庆在楼上喝茶，仆人报信后翻窗逃走，而《水浒传》里武松直接砍了头。
-- **发言人1**：武松报仇总被打压下去，被高官权势摁压，之后被发配，故事转而讲西门庆的线。
-- **发言人2**：概括为「西门庆霸凌武大郎」。
-- **发言人3**：称《金瓶梅》是西门庆这个小人物的发展史，与《水浒》起义章节不同。
-- **发言人4**：提到西门庆最后跟童贯还是谁攀上中央的线，「当地一霸」。
-- **发言人2**：询问西门庆与宋江等人有无交集，发言人3回应应该不会写，但丞相是同一个。
-- **发言人2**：询问西门庆结局，发言人3称在《金瓶梅》版本里是纵欲过度而死，与《水浒传》中被砍头不同。
-- **发言人3**：西门庆有十个老婆，有的懦弱，潘金莲属于很有心机、比较强势的那一种。
-- **发言人3**：记得西门庆有一个老婆生病后去看和尚、不去治病，信迷信而死；还提到书里佛教很黑，收灯油钱。
-- **发言人4**：称《金瓶梅》比《红楼梦》接地气，吃的也写得好，西门庆摆宴的描写很精彩。
-## 《西游记》中佛教的虚伪
-- **发言人1**：提到如来佛祖帮一个国家后收了300两黄金，说「区区300两黄金」。
-- **发言人2**：记得两个体现佛教虚伪的情节——狮驼岭，以及唐僧单独取经时寄宿寺院，住持贪唐僧袈裟，引火把自己烧死。
-- **发言人4**：提到《黑神话》里也有相关boss。
-## 《红楼梦》的历史背景
-- **发言人2**：询问《红楼梦》在历史上有没有真实发生的历史事件，对比三国、水浒有明确历史人物和时间线。
-- **发言人3**：回应《红楼梦》没有明确朝代，是写得很虚的故事。
-- **发言人4**：称作者是那个时代的，就是映射那个时代；有说法认为演的是曹雪芹的经历，他以前好像是个大家族。
-- **发言人3**：认同，称要不然写不出那么多细节。
-- **发言人1**：补充《红楼梦》当时是禁书，不说朝代已是禁书，说朝代更禁。
+## 红楼梦四大家族与官场暗线
+- **发言人3**：提出《红楼梦》有一条官场暗线，即朝堂政权变化与四大家族兴衰交织；王熙凤前期地位高、后期结局惨，与其兄长在官场上的地位及先死直接相关，并称「有人研究这条暗线」。
+- **发言人4**：质疑四大家族「感觉就没几个人」，每家只登场两家人多一点，王熙凤家、史家、薛宝钗家都只见典型人物，书里人也不多，薛宝钗家「没什么靠山」。
+- **发言人3**：回应薛宝钗家是做生意的，有钱但无官场靠山。
+- **发言人1**：背诵护官符诗句——「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」。
+- **发言人4**：认为护官符把四大家族说得「都很牛逼」，但实际「就感觉没什么厉害人家」。
+- **发言人3**：总结四大家族整体都在走下坡路。
+- **发言人1**：认同此说，认为写的就是王朝家族的衰败。
+## 红楼梦细节与版本
+- **发言人4**：提到小时候看《红楼梦》印象最深的是吃螃蟹非常讲究，要「又卸钳又卸身」，第一次知道吃螃蟹需要这么多工具；还提到尼姑庵泡茶的水特别讲究。
+- **发言人3**：补充冷香丸的制作——需雨水那一日的雨水、小雪那一日的雪，每个节气都要正好碰上；**发言人1**补充需春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
+- **发言人3**：提到120回版本中薛宝钗嫁给贾宝玉，但好多人说是无性婚姻，因贾宝玉不久就出家；另有一个版本写薛宝钗后来怀了孩子，但「那肯定是狗血版本」。
+- **发言人2**：追问孩子是贾宝玉的吗，**发言人3**回应那是狗血版本，**发言人1**认为「不至于弄这么狗血」。
+## 金瓶梅与水浒传的关系
+- **发言人1**：讲述《金瓶梅》从武松杀武大郎之后开始写；武松找西门庆报仇时，西门庆在楼上喝茶，仆人报信后翻窗逃走，原《水浒传》里没有翻窗、直接砍头，金瓶梅里翻窗后武松报仇不了，被发配，之后开始讲西门庆的线。
+- **发言人1**：指出武松报仇总被打压下去，被高官、大家族、权势摁压下来，所以「就很真实」。
+- **发言人3**：认为《金瓶梅》就是西门庆这个小人物的发展史，一个无赖能爬到比较高、过得比较舒服，写的是官场如何黑。
+- **发言人4**：提到西门庆跟中央（童贯还是谁）攀上线，「当地一霸」；还提到金瓶梅里吃的也写得好，西门庆摆宴。
+- **发言人2**：询问西门庆与宋江等人有无交集，**发言人3**回应应该不会写，但「丞相是同一个」。
+- **发言人2**：询问西门庆结局在两个版本中的差异，**发言人3**回应金瓶梅版本中西门庆是「终于过度死」（重病昏过去而死），水浒传版本中被砍头。
+- **发言人3**：提到西门庆有约十个老婆，有的老婆特别懦弱，潘金莲属于很有心机、比较强势的那一种；还提到一个老婆生病后去看和尚、不去治病，信迷信而死。
+- **发言人4**：确认潘金莲属于强势老婆，并追问武大郎是否也死在潘金莲手下，**发言人3**回应前面应该差不多。
+## 西游记中的佛教虚伪
+- **发言人1**：提到如来佛祖帮一个国家后，说「区区收了300两黄金」，体现佛教虚伪。
+- **发言人2**：补充两个例子——狮驼岭；孙悟空和唐僧单独取经时寄宿寺院，住持有很多袈裟、觊觎唐僧袈裟，后来引火把自己烧死。
+- **发言人4**：提到黑神话游戏里也有相关boss（金齿蟑螂）。
+## 历史背景与映射
+- **发言人2**：询问《红楼梦》在历史上有没有真实发生的历史事件，并指出三国、水浒有明确历史人物和时间线，水浒和金瓶梅是同时期真实发生的事。
+- **发言人3**：回应《红楼梦》没有明确朝代，开头湖边漫步，写得很虚。
+- **发言人4**：认为作者是那个时代的，就是映射那个时代；有说法说红楼梦演的就是曹雪芹的经历，他以前好像是个大家族。
+- **发言人1**：补充《红楼梦》当时是禁书，不说朝代，说朝代更禁。
+- **发言人3**：认为曹雪芹若不是大家族出身，写不出那么多细节（吃螃蟹技巧、冷香丸等）。
 ## 东吴二宫之争
-- **发言人2**：介绍孙权二宫之争，太子孙登与鲁王两派，不同大臣支持不同儿子；孙权老婆王夫人与女儿孙鲁班有心机，一起反杀，把东吴政局搅得一团糟。
+- **发言人2**：提到孙权二宫之争，太子孙登与鲁王两派大臣各支持一方；孙权的老婆王夫人与女儿孙鲁班有心机，一起反杀，把东吴政局搅得一团糟，并询问大家了解多少。
 # 共识形成
-- **一致意见**：本场为自由漫谈，未形成正式决议或统一结论，但就多个话题形成了倾向性认识。关于《红楼梦》，发言人3提出存在**官场暗线**，四大家族兴衰与官场地位相关，如王熙凤前期地位高与其兄长在官场地位相关、结局惨因其兄长先死，发言人1补充护官符诗句「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」佐证四大家族（贾、史、王、薛）的权势设定，发言人4质疑「四大家族感觉就没几个人」，发言人3以薛宝钗家有钱、做生意回应，并指出「他们整体都在走一个下坡路」，发言人1认同「说的就是王朝家族的衰败」。
-- **倾向性认识**：关于《金瓶梅》与《水浒传》关系，发言人1介绍《金瓶梅》从武松杀西门庆失败后开始写，武松报仇被高官权势压制、西门庆翻窗逃走，而《水浒传》中武松直接砍头；发言人3称西门庆是「小人物发展史」，其结局在金瓶梅中为纵欲过度而死，西门庆与宋江等人无交集但丞相是同一个。关于《红楼梦》历史背景，发言人3称「没有明确的朝代，就是一个写的很虚的故事」，发言人4提到有说法映射曹雪芹经历，发言人1补充「红楼梦当时不是禁书吗？都已经不说朝代已经是禁书了」。
-- **主要分歧点**：关于薛宝钗婚后是否怀孕，发言人3称「120回那一集里面的版本」为无性婚姻、贾宝玉不久出家，但「后来好像又怀了一个孩子」，随即自认「那肯定是狗血版本」，发言人1回应「这个应该不至于弄这么狗血」，发言人2质疑「那是贾宝玉的还是」，未达成一致。关于《金瓶梅》中武松报仇线，发言人1称有报仇线但「没有报仇成功」，发言人4称西门庆「最后死是因为重病昏过去了」，与发言人3所述「纵欲过度而死」口径略有出入，未进一步核实。
+- **一致意见**：与会者普遍认可《红楼梦》存在官场暗线，四大家族（贾、史、王、薛）的兴衰与官场地位相关，整体呈走下坡路态势，象征王朝家族衰败；《金瓶梅》与《水浒传》同属北宋背景，但《金瓶梅》从武松杀武大郎之后写起，聚焦西门庆这一小人物的发迹史。
+- **倾向性认识**：关于《金瓶梅》中武松报仇线，发言人1指出其报仇未成功、被高官权势打压，与《水浒传》中直接砍头不同，西门庆翻窗逃走、武松被发配，此后转入西门庆主线；发言人3补充西门庆与宋江等人无交集，但丞相为同一人。
+- **主要分歧点**：关于薛宝钗婚后结局，发言人3提到120回版本中贾宝玉出家、有说法称无性婚姻，另有版本称薛宝钗怀孕，但发言人3本人认为该说法属「狗血版本」，发言人1亦表示「不至于弄这么狗血」；关于《红楼梦》朝代背景，发言人3认为其无明确朝代、写得很虚，发言人4则主张其映射明末清初时代，且有说法映射曹雪芹经历。
 # 待探讨问题与后续
-- **未确认**：《红楼梦》中四大家族是否人少，发言人4质疑四大家族感觉没几个人，每家就两家人多一点，发言人3未正面回应，仅解释薛宝钗家有钱、是做生意的。
-- **未确认**：《金瓶梅》中武松报仇线是否成功，发言人1称武松报仇总是被打压下去，被高官权势摁压下来，未提及最终是否成功。
-- **未确认**：《金瓶梅》中潘金莲是否属于强势老婆，发言人3称潘金莲属于很有心机、比较强势的那一种，发言人4表示认同，但未展开论证。
-- **待核实**：《金瓶梅》中一个老婆是否因迷信而死，发言人3称记得有一个老婆生病后去看和尚、不去治病，回来死了，发言人4表示细节记不清。
-- **待核实**：《西游记》中如来佛祖收300两黄金是哪一章节，发言人1称好像是最后一集，但记不清具体章节。
-- **未定论**：《红楼梦》是否映射曹雪芹经历，发言人4提到有说法称《红楼梦》演的就是曹雪芹的经历，发言人3称要不然写不出那么多细节，但未达成一致结论。
-- **未定论**：薛宝钗与贾宝玉婚姻是否为无性婚姻，发言人3称有版本说贾宝玉不久出家、是无性婚姻，另有版本称薛宝钗后来怀了孩子，但被认定为狗血版本，发言人1表示不至于弄这么狗血。
-- **未确认**：《金瓶梅》中西门庆与宋江等人是否有交集，发言人1称不知道，发言人3称应该不会写，但丞相是同一个。
-- **未确认**：《金瓶梅》中宰相或丞相的最后结局，发言人3称只看了一点、没看结局，发言人4称忘了。
-- **未确认**：《金瓶梅》中一个老婆是否因迷信而死，发言人3称记得有一个老婆生病后去看和尚、不去治病，回来死了，发言人4表示细节记不清。
-- **未确认**：《西游记》中如来佛祖收300两黄金是哪一章节，发言人1称好像是最后一集，但记不清具体章节。
-- **未确认**：《红楼梦》是否映射曹雪芹经历，发言人4提到有说法称《红楼梦》演的就是曹雪芹的经历，发言人3称要不然写不出那么多细节，但未达成一致结论。
-- **未确认**：薛宝钗与贾宝玉婚姻是否为无性婚姻，发言人3称有版本说贾宝玉不久出家、是无性婚姻，另有版本称薛宝钗后来怀了孩子，但被认定为狗血版本，发言人1表示不至于弄这么狗血。
-- **未确认**：《金瓶梅》中西门庆与宋江等人是否有交集，发言人1称不知道，发言人3称应该不会写，但丞相是同一个。
-- **未确认**：《金瓶梅》中宰相或丞相的最后结局，发言人3称只看了一点、没看结局，发言人4称忘了。</t>
+- **未确认**：《金瓶梅》中宰相（蔡京）的最终结局，发言人3表示只看了一点，发言人4也记不清。
+- **未确认**：《红楼梦》是否映射曹雪芹个人经历，发言人4提到有这种说法，但未获证实。
+- **未确认**：东吴二宫之争的具体细节，发言人2提出话题后因时间原因未展开讨论。
+- **未定论**：薛宝钗与贾宝玉婚后是否怀孕，发言人3提到有版本称其怀孕，但认为属狗血版本，发言人1也表示不至于如此。
+- **待核实**：《西游记》中如来佛祖收300两黄金的章节出处，发言人1表示记不清是哪一集。
+- **待核实**：《金瓶梅》中西门庆一个老婆因迷信和尚不治病而死的情节，发言人3记得此事，发言人4表示细节记不清。
+- **未定论**：《红楼梦》四大家族是否真如护官符所形容那般显赫，发言人4质疑「感觉没什么厉害人家」，发言人3认为整体在走下坡路。</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>48.1</v>
+        <v>54.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5893/3703</t>
+          <t>5893/2955</t>
         </is>
       </c>
     </row>
@@ -15238,40 +15078,43 @@
       <c r="C43" t="inlineStr">
         <is>
           <t># 全文摘要
-会议前半段为多人闲聊，围绕小说、综艺、专业背景与洗发水等话题展开。发言人1表示看过《红楼梦》多遍，高中时读不太懂，反复读才发现有意思；发言人2不怎么看小说，刷短剧较多，平时看电视剧和综艺。发言人1提到《种地吧》综艺，十个男孩子大部分搞音乐，录制周期半年、几乎24小时录制，成员成立农业公司发展新型农业，种小月季和水培蔬菜，项目有亏有盈，成员是实际股东每人掏钱，个人挣钱主要靠综艺。发言人1还提到英国综艺《克拉克森的农场》。专业背景方面，发言人2是俄语专业但就业未往俄语方向，56年没用已忘记；发言人1学数学和统计，发言人4学软件工程。洗发水话题中，发言人4表示换用多种洗发水，头发不易油。
-会议后半段转入日本现代化转型话题。发言人5提到下一个是陆小薇的中英混播，发言人6建议谈日本的现代化转型，涉及明治维新和和平宪法。发言人5表示自己不懂，发言人6提到彪子在日本上学是主场，但彪子也表示不太懂。随后讨论录制安排，涉及八爪鱼、金融等，小辉是中央会，八爪鱼是为了金融，让他走了不着急。整体以分享为主，未形成明确结论。
+这是一场多人参与的闲聊式会议录音，参与方为六位发言人（发言人1至发言人6），无明确主办方与机构背景。会议前半段围绕个人阅读与观影偏好展开，涉及小说、短剧、综艺等话题；后半段转入录制安排，确定下一期主题。闲聊部分覆盖阅读习惯（发言人1多次阅读《红楼梦》、发言人2主要刷短剧）、综艺讨论（重点介绍《种地吧》与英国综艺《克拉克森的农场》）、个人专业背景（俄语、数学统计、软件工程）及洗发水使用习惯等板块。录制安排部分确定下一期主题为日本的现代化转型，涉及明治维新与和平宪法，由陆小薇负责中英混播，全员参与录制。关键结论为下一期主题确定为日本的现代化转型，其余以分享为主，未形成明确结论。关键数字包括：《种地吧》录制周期约半年、几乎24小时录制；发言人2称俄语56年未用已遗忘；发言人4囤有三种洗发水换用。
 # 分段速览
-## 00:00:02-00:06:06 闲聊：小说与综艺
-开场后发言人1询问大家是否看小说，发言人2表示不怎么看，刷短剧较多。发言人1提到自己反复阅读《红楼梦》多遍，高中时读不太懂，后来才体会到趣味。话题随后转向综艺，发言人2与发言人4表示平时看电视剧和娱乐综艺较多，发言人4偏好旅游类和户外类。发言人1介绍《种地吧》综艺，十个男孩子多为音乐出身，录制周期约半年、几乎24小时拍摄，成员成立农业公司发展新型农业，种小月季和水培蔬菜，项目有亏有盈，成员为实际股东、每人出资，个人收入主要靠综艺；另提及英国综艺《克拉克森的农场》。发言人4询问录制周期与收益模式，发言人1逐一回应，并说明种月季需请专人看护水土，农业门槛较高。
-## 00:06:06-00:10:13 闲聊：专业背景与洗发水
-发言人1得知发言人2为俄语专业，发言人2表示就业未往俄语方向，五六年未用已遗忘。发言人2提到康鹏曾科普俄罗斯人做生意的情况，称其贸易多内部消化、对外营销较少。发言人1介绍自己学数学和统计，发言人4学软件工程，属工科。随后话题转到头发，发言人4分享自己换用多种洗发水，家中囤有三种轮换使用，头发不再容易出油；发言人2询问品牌，发言人4表示记不清名称，答应之后查订单告知。
-## 00:10:13-00:13:02 录制安排与日本现代化转型话题
-发言人1结束录播后，发言人5接手，提到下一个是陆小薇的中英混播。发言人6建议谈日本现代化转型，涉及明治维新与和平宪法，发言人5表示自己不懂该话题。发言人6提到彪子在日本上学、应是主场，但彪子也表示不太懂。随后讨论录制安排：小辉是中央会，八爪鱼为金融相关，已让其离开不着急录制；发言人5提到三楼有空会议室，准备去那边继续。
+## 00:00:02-00:06:06 闲聊：阅读与综艺
+发言人1询问大家是否看小说，发言人2表示不看小说、主要刷短剧，发言人1提到自己反复阅读《红楼梦》多遍，发言人2误以为指网文。话题转向综艺，发言人1介绍《种地吧》由十个男孩参与，录制周期约半年、几乎24小时录制，成员成立农业公司并实际出资，种植小月季和水培蔬菜，项目有盈有亏；还提及英国综艺《克拉克森的农场》。发言人4表示看综艺较多，偏好旅游类和户外类。
+## 00:06:23-00:10:13 闲聊：专业背景与洗发水
+发言人2称自己是俄语专业但就业未从事俄语，56年未用已遗忘，并提到康鹏曾科普俄罗斯贸易相关信息但不外传。发言人1表示曾学数学、后学统计，发言人4为软件工程专业。随后聊到洗发水，发言人4称换用三种产品后头发不易出油，发言人2询问推荐品牌，发言人4表示记不清牌子、稍后找订单告知。
+## 00:10:22-00:13:02 录制安排与下期主题
+发言人1表示录播结束，发言人5确认上一期已全部录完，提出下一期由陆小薇负责中英混播。发言人6建议主题为日本的现代化转型，涉及明治维新与和平宪法，并指出彪子在日本上学、可作为主场，但彪子表示不懂。发言人5确认全员参与录制，并提及八爪鱼、小慧等录制安排，其中八爪鱼与金融相关。最终确定下一期主题为日本的现代化转型。
 # 要点梳理
 ## 闲聊话题
-- **小说阅读**：发言人2表示不怎么看小说，刷短剧较多；发言人1看过《红楼梦》很多遍，高中时读不太懂，反复读才发现有意思。
-- **综艺偏好**：发言人2和发言人4看电视剧和综艺多一点，发言人4偏好旅游类和户外综艺，发言人2提到做饭类综艺。
-- **《种地吧》**：发言人1看过该综艺，十个男孩子大部分搞音乐，走小众路线，后来组成组合、开演唱会，粉丝较多。
-- **《种地吧》录制**：录制周期半年，几乎24小时录制，视频素材多；成员成立农业公司，发展新型农业，种小月季和水培蔬菜。
-- **《种地吧》收益**：项目有亏有盈，成员是实际股东、每人掏钱；个人挣钱主要靠综艺，节目里讲农业怎么挣钱。
-- **《种地吧》养殖**：有一个鱼塘，但可能没有认真搞；种月季需请专人看水和土，农业门槛高。
-- **《克拉克森的农场》**：发言人1提到英国种地综艺《克拉克森的农场》，认为挺好看。
-- **三农主题**：发言人1表示最近三农主题较多，挺多人喜欢看。
-- **专业背景**：发言人2是俄语专业，但就业未往俄语方向，56年没用已忘记；发言人1学数学和统计，发言人4学软件工程。
-- **俄语贸易**：发言人2提到北方可能用到俄语做贸易，康鹏曾科普过俄罗斯人做生意的事，但内部消化较多、对外营销较少。
-- **洗发水话题**：发言人4换用多种洗发水，家里囤三种轮着用，头发没那么容易油；发言人2询问推荐，发言人4表示找到订单后告知牌子。
-## 日本现代化转型
-- **话题提出**：发言人6建议谈日本的现代化转型，涉及明治维新和和平宪法。
-- **参与情况**：发言人5表示自己不懂日本现代化转型；发言人6提到彪子在日本上学是主场，但彪子也表示不太懂。
-- **录制安排**：发言人5提到下一个是陆小薇的中英混播；小辉是中央会，八爪鱼是为了金融，让他走了不着急。</t>
+- **阅读偏好**：发言人1表示看过《红楼梦》很多遍，高中初读时不太能读懂，反复读后才觉得有意思；发言人2表示不看小说、主要刷短剧，误以为发言人1说的是网文。
+- **综艺偏好**：发言人2看电视剧和综艺较多，发言人4看娱乐综艺较多，烧脑类看得少；发言人1表示工作已够费脑，休息时间喜欢娱乐类内容。
+- **《种地吧》**：发言人1介绍该综艺为十个走偶像路线的男孩子参与，大部分搞音乐，录完后组成组合并开演唱会，粉丝较多。
+- **《种地吧》录制**：几乎24小时录制，一录半年，视频素材特别多；成员种小月季和水培蔬菜，种月季时需请专人看水和土，外行人很难操作。
+- **《种地吧》经营**：成员成立农业公司，作为实际股东每人掏钱，投多个项目，有的亏钱、有的盈利；个人挣钱主要靠综艺，节目内以农业主题讲农业怎么挣钱。
+- **《克拉克森的农场》**：发言人1提及看过英国种地综艺《克拉克森的农场》，也挺好看。
+- **三农主题**：发言人1表示最近三农主题内容比较多，挺多人喜欢看。
+- **专业背景**：发言人2为俄语专业，就业时未从事俄语相关工作，56年没用已遗忘；发言人1之前学数学、后学统计；发言人4为理科生，学软件工程（工科）。
+- **俄语贸易**：发言人2称北方可能用得上俄语做贸易，康鹏曾科普过俄罗斯人主要做什么生意，但贸易相关信息不怎么外传、内部消化较多，往外营销做得少。
+- **洗发水习惯**：发言人4洗发水换着用，现囤三种轮着用，称之前头发容易油或痒，换用后没那么容易油了；发言人2听说换着用对头发好，发言人1提到避免只用一种导致酸碱偏了。
+- **洗发水品牌**：发言人4所用品牌是不认识的外国牌子，记不住名字，答应之后找订单告诉发言人2。
+## 录制安排与主题确定
+- **上期录制**：发言人5确认上一期已全部录完，发言人1表示先停录。
+- **下期主题**：发言人5提出下一期由陆小薇负责中英混播；发言人6建议主题为日本的现代化转型，涉及明治维新与和平宪法。
+- **主场人选**：发言人6指出彪子在日本上学、是主场，但彪子表示对日本现代化不太懂。
+- **录制安排**：发言人5提及八爪鱼、小慧等录制安排，八爪鱼与金融相关，小慧是八爪鱼同性别；确认全员参与录制。
+- **场地安排**：发言人1去三楼找会议室，发言人5提到三楼有空会议室。
+## 结论与决定
+- **下期主题确定**：确定下一期主题为日本的现代化转型，由陆小薇负责中英混播，全员参与录制。</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5310/2001</t>
+          <t>5310/1996</t>
         </is>
       </c>
     </row>
@@ -15428,84 +15271,88 @@
       <c r="C44" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讲座由主讲人（原文未提及姓名及机构头衔）围绕朝鲜战争历史展开讲解，以口述形式梳理朝鲜半岛从分裂到统一再到分裂的进程，并面向听众开放自由提问。讲座覆盖战争爆发背景、各方称谓、重要战役、停战协定、战争影响、朝韩现状、朝鲜旅游、半岛分裂渊源、当前朝韩关系、中俄朝关系、韩军作用及抗美援朝决策原因等板块。主讲人核心判断包括：朝鲜战争奠定了中国的强国地位，美国不敢再小瞧中国；朝韩若统一大概率是韩国兼并朝鲜，但对东北亚地区是“不稳定的定时炸弹”；韩军战斗力在1952年前“不敢恭维”，1952年后“不可小视”。关键锚点包括：1950年6月战争爆发、1953年7月27日停战协定、三八线及北纬十七度线。讲座对理解朝鲜战争历史脉络及当前东北亚局势具有参考意义，适用对象为对朝鲜战争及半岛问题感兴趣的听众。
+本次研讨会由主讲人系统讲解朝鲜战争历史，围绕战争背景、进程、影响及当前朝韩关系展开，并回答听众提问。1945年二战结束，美苏军队以北纬38度为基准分驻朝鲜南北，形成三八线；1949年新中国宣布废除列强在华特权，收回苏联在东北的中长铁路及大连旅顺特区，苏联遂鼓动朝鲜进攻韩国。1950年6月朝鲜战争爆发，朝鲜称“祖国统一解放战争”，中国称“抗美援朝”，韩国称“625事件”，美国称“朝鲜战争”或“韩战”。朝鲜人民军一度打到洛东江环形防御圈（大邱至釜山一带），1950年9月15日美军仁川登陆成功，分割包围朝鲜人民军；联合国军由美军主导，共16国出兵，麦克阿瑟任总司令。中国以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩军首次交火，11月5日第一次战役结束；此后历经长津湖战役（第二次战役）、第三次战役（越过三八线占领汉城、仁川、水源，扩展至三七线），第五次战役为最后一次大规模战役，双方在三八线互有攻防。1953年7月27日双方达成停战协定，朝韩名义上停战，未实现真正和平，边界大致沿三八线形成，延续至今。
+主讲人从中国、美国、朝韩三方角度分析战争影响：从中国角度，战争奠定了强国地位，美国再不敢小瞧，1967年越南战争时期中国警告美国不得越过北纬十七度线，美国未敢越过；美国称朝鲜战争为“被遗忘的战争”，最后一任司令官马克·克拉克承认是美国历史上第一次在未取得胜利情况下签署停战协定；伤害最深的是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线悲剧延续至今。
 # 核心观点与论证
-## 论点：朝鲜战争爆发背景与各方称谓
-- **历史根源**：1945年日本投降后，美苏军队分别进驻朝鲜南北，以北纬38度为基准形成三八线；1949年新中国宣布废除列强在华一切租界及特权，包括苏联在东北的`中长铁路`及大连旅顺特区，苏联不甘心，鼓动朝鲜进攻韩国，希望以仁川或釜山替代旅顺大连地位，继续在亚洲发挥影响力。
-- **战争爆发**：1950年6月，北朝鲜军队率先越过三八线向南进攻，朝鲜战争爆发；各方称谓不同——朝鲜称`祖国统一解放战争`，中国称`抗美援朝`，韩国称`625事件`，美国及西方称`朝鲜战争`或`韩战`（台湾地区称谓）。
-- **初期战况**：战争开始后，朝鲜人民军从三八线打到`洛东江环形防御圈`（大邱到釜山一带）；1950年9月15日美军在仁川登陆成功，将深入韩国境内的朝鲜人民军分割包围、逐次歼灭，收复三八线以南领土。
-## 论点：中国出兵与主要战役进程
-- **出兵决策**：美军以联合国军身份参战（共16国出兵），总司令麦克阿瑟想扩大战果吞并整个北朝鲜；中国因朝鲜半岛`唇亡齿寒`，决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩军首次交火，11月5日第一次战役结束。
-- **战役推进**：第二次战役即`长津湖战役`（国内影视作品近年宣传较多）；第三次战役越过三八线，占领汉城（今首尔）、仁川、水源一带，疆域扩展到`三七线`（北纬37度）；此后美军反攻，双方在三八线与三七线之间鏖战。
-- **停战协定**：第五次战役（最后一次大规模战役）后，双方在三八线互有攻防：西部中朝方面占领开城、延安半岛、望京半岛；东部美军占领襄阳、金刚山地区（金刚山今为韩国著名旅游景点）；1953年7月27日双方正式达成停战协定，朝韩仅名义停战，未实现真正和平，三八线非军事区（DMZ）成为今日边界与旅游景点。
-## 论点：朝鲜战争的影响与意义
-- **中国地位**：朝鲜战争奠定了中国的强国地位，美国再不敢小瞧中国；1967年越南战争时期，中国警告美国绝对不允许越过`北纬十七度线`（南越与北越边境线），否则中国必将出兵越南，美国未敢越过。
-- **美国视角**：美国称朝鲜战争为`被遗忘的战争`；最后一任司令官马克·克拉克承认，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。
-- **朝韩悲剧**：伤害最深的还是朝鲜和韩国——本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
-## 论点：朝鲜半岛分裂的历史渊源
-- **大国意图**：美国和苏联都希望在朝鲜半岛建立缓冲区——美国为保护日本免遭苏联及共产主义势力影响，在南方单独建立韩国；苏联需要在亚洲建立卫星附属国，扶植北朝鲜，奉行对苏联马首是瞻的指示。
-- **统一计划落空**：最初计划像奥地利那样在不同占领区受降后举行普选、建立统一民选政府；但美苏关系恶化急转直下，所扶植的领导人各有心思，因意识形态不同最终建立两个国家，这也是朝鲜战争爆发的缘由。
-## 论点：当前朝韩关系与统一展望
-- **美国态度**：美国因惧怕朝鲜背后的中国和俄罗斯，未主动进攻朝鲜或再次挑起半岛武装冲突——朝鲜战争时中国出动志愿军把美军打回去，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南；朝鲜金家也担心江山被颠覆，不敢贸然发动战争。
-- **统一形态**：若朝韩统一，**大概率是韩国兼并朝鲜**——经济影响和综合实力摆在那儿；北方有充足优质兵源及核武器、导弹等尖端武器，统一后对东北亚地区是**不稳定的定时炸弹**。
-- **历史参照**：越南统一后第二年即进攻柬埔寨和泰国，中国1979年出兵对越南发动自卫反击战；越南尚且如此，朝鲜半岛统一后局势更加不可控。
-## 论点：中俄朝关系与图们江出海口问题
-- **关系现状**：中国、俄罗斯和朝鲜之间`各怀鬼胎`；图们江出海口问题至今拖着没有着落——图们江是俄罗斯和朝鲜的界江，是日本海出海口，中朝俄边境国际水域航道可通行，但俄朝建了一座小桥，大船无法通过。
-- **原因分析**：俄罗斯和朝鲜都不希望中国过分强大、不想过多依附中国，所以封死图们江出海口，不想把出海口让给中国。
-## 论点：韩军在朝鲜战争中的作用与评价
-- **初期表现**：战争初期韩军瞎指挥，差点被朝鲜团灭；6月25日战争爆发后，7月10日起南部地面战斗主要是美军和朝鲜人民军进行，韩军负责`冲人头`角色；1952年美国重新整军训练后，韩军才形成基本战斗力。
-- **中期拖累**：1952年之前韩军对美军像`猪队友`——志愿军与美军占不到便宜时，都从韩军战线突击，美军每次兵败都是韩军战线崩溃引起；第五次战役中志愿军从朝鲜半岛东部形成反包围突击，打崩韩军前线，美国在韩国领土上把`韩国第三军团`全部撤销。
-- **军队文化**：韩军军官主体是二战时期日本人扶植的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁强征的农村青年；韩军从成军至今贯彻昭和日军`武士道精神`管理体制，老兵欺负新兵、军队霸凌事件延续至今屡见不鲜；**1952年前战斗力不敢恭维，1952年后不可小视**。
-## 论点：抗美援朝而非收复台湾的决策原因
-- **海军制约**：台湾与大陆之间海峡距离约100公里，中共刚建国没有相应海军实力，无法进行解放台湾的战斗；1950年朝鲜战争爆发后，美国参众两院视为共产主义世界对自由世界的全面进攻，将台湾和韩国共同纳入亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。
-- **战略选择**：美国越过三八线向中朝边境进发，触动中国敏感神经，`唇亡齿寒`深入人心；即便不愿与美国爆发全面战争，又不得不打——解放军陆军很强，海上无法战斗，只能在陆地战斗，索性争取战略主动；长津湖和上甘岭两场战役接连让美军惨败，至今是美国人挥之不去的梦魇。
+## 论点：朝鲜半岛分裂与朝鲜战争爆发源于美苏冷战布局与新中国废除苏联在华特权
+- **分裂起点**：1945年二战结束、日本投降后，美苏军队分别进驻朝鲜南北，以北纬38度为基准形成三八线；1949年新中国宣布废除列强在华一切租界及特权，包括苏联在东北的`中长铁路`及大连旅顺特区，苏联不甘心失去利益，鼓动朝鲜进攻韩国，希望以仁川或釜山替代旅顺、大连地位。
+- **战争爆发与各方称谓**：1950年6月北朝鲜军队率先越过三八线南攻，朝鲜称`祖国统一解放战争`，中国称`抗美援朝`，韩国称`625事件`，美国及西方国家称`朝鲜战争`或`韩战`（台湾地区称谓）。
+- **初期战局与美军介入**：朝鲜人民军从三八线打到`洛东江环形防御圈`（大邱至釜山一带）；1950年9月15日美军在仁川登陆成功，分割包围并逐次歼灭朝鲜人民军，收复三八线以南领土；联合国军由美军主导、16国共同出兵，麦克阿瑟任总司令并试图吞并整个北朝鲜。
+## 论点：中国以志愿军形式出兵抗美援朝，历经五次战役后于1953年停战
+- **出兵与首战**：美军越过三八线触动中国`唇亡齿寒`神经，1950年10月19日志愿军跨过鸭绿江，10月25日与韩军首次交火，11月5日第一次战役结束。
+- **关键战役**：第二次战役即长津湖战役（近年国内影视作品宣传）；第三次战役越过三八线，占领汉城（今首尔）、仁川、水源，扩展至三七线（北纬37度）；第五次战役为最后一次大规模战役，双方在三八线互有攻防。
+- **停战与边界**：西部中朝占领开城、延安半岛、望京半岛，东部美军占领襄阳、金刚山地区；1953年7月27日双方达成停战协定，朝韩名义上停战、未实现真正和平，边界大致沿三八线形成延续至今。
+## 论点：朝鲜战争奠定中国强国地位，对美国是未胜利的停战，对朝韩是分裂悲剧
+- **中国地位**：战争奠定中国强国地位，美国再不敢小瞧；1967年越南战争时期中国警告美国不得越过北纬十七度线（南越与北越边境线），美国未敢越过。
+- **美国视角**：美国称朝鲜战争为`被遗忘的战争`，最后一任司令官马克·克拉克承认是美国历史上第一次在未取得胜利情况下签署停战协定的司令官。
+- **朝韩悲剧**：伤害最深的是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线悲剧延续至今。
+## 论点：朝鲜半岛分裂源于美苏冷战与意识形态对立，统一后可能成为不稳定因素
+- **分裂渊源**：美苏都希望在朝鲜半岛建立缓冲区——美国为保护日本免遭苏联及共产主义势力影响而建立韩国，苏联为建立亚洲卫星附属国支持北朝鲜；最初计划像奥地利一样普选建立统一民选政府，但美苏关系急转直下、扶植的领导人各有心思，最终建立两个国家。
+- **当前平衡**：美国因惧怕朝鲜背后的中国和俄罗斯（朝鲜战争时中国出动志愿军、苏联提供空军掩护和武器后勤支持）而未主动进攻朝鲜；金家也担心江山被颠覆，不敢贸然发动战争，形成微妙平衡。
+- **统一展望**：朝韩若统一大概率是韩国兼并朝鲜（经济影响和综合实力占优），但北方有充足优质兵源及核武器、导弹等尖端武器，统一后对东北亚是`不稳定的定时炸弹`；主讲人以越南为鉴——越南统一后第二年进攻柬埔寨和泰国，被中国1979年出兵自卫反击，朝鲜半岛统一后局势更不可控。
+## 论点：韩军在朝鲜战争中前期战斗力弱，1952年后经美军整训才形成基本战斗力
+- **前期表现**：战争初期韩军瞎指挥、差点被朝鲜团灭；1950年6月25日战争爆发后，7月10日以后南部地面战斗主要是美军与朝鲜人民军进行，韩军只负责`冲人头`角色；志愿军与美军占不到便宜时常从韩军战线突击，美军每次兵败都由韩军战线崩溃引起。
+- **转折点**：1952年美国对韩国整军训练备战后，韩军才形成基本战斗力；第五次战役中志愿军从朝鲜半岛东部反包围突击打崩韩军前线，美军在韩国领土上撤销了韩国第三军团。
+- **军队构成与思想**：韩军军官主体是二战时期日本人扶植的伪军和傀儡部队骨干，士兵类似国民党抓壮丁形式强征农村青年；贯彻昭和日军武士道精神管理体制，`关西兵`、老兵欺负新兵，军队霸凌事件蔓延至今，是旧日军部队的延伸。
+## 论点：中国选择抗美援朝而非收复台湾，源于海军实力不足与唇亡齿寒的战略考量
+- **无法收复台湾**：台湾与大陆海峡距离约100公里，中共刚建国没有相应海军实力；1950年朝鲜战争爆发后，美国参众两院视为共产主义对自由世界的全面进攻，将台湾和韩国纳入亚太保护圈，美军陆军出兵朝鲜半岛、海军第七舰队进驻台湾，既防解放军解放台湾也防国民党反攻大陆。
+- **必须出兵朝鲜**：美国越过三八线向中朝边境进发，触动中国敏感神经，`唇亡齿寒`深入人心；解放军陆军很强，海上无法战斗就只能在陆地战斗，长津湖和上甘岭两场战役接连让美军惨败，成为美国人挥之不去的梦魇。
+## 论点：中俄朝关系各怀鬼胎，图们江出海口问题至今未解决
+- **图们江出海口**：图们江是俄罗斯和朝鲜的界江、日本海出海口，中朝俄边境国际水域航道可通行，但俄罗斯和朝鲜建了一座小桥，大船无法通过，封死出海口；俄罗斯和朝鲜都不希望中国过分强大，不想把出海口让给中国，问题至今拖着没有着落。
 # 金句总结
-&gt; 朝鲜战争在美国被称为“被遗忘的战争”，因为联合国军最后一任司令官马克·克拉克承认，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。
-&gt; 唇亡齿寒这个概念深入人心，所以说导致了即便不愿意和美国爆发全面战争，但是又不得不进行一个全面战争。
-&gt; 朝鲜和韩国本就是血肉同胞，却分裂成了两个国家，并且这样的三八线的悲剧延续至今。
+&gt; 朝鲜半岛对于中国的意义来说，就是一个唇亡齿寒的一个状态。
+- 背景：主讲人解释美军越过三八线后中国决定出兵的原因，强调朝鲜半岛对中国的地缘安全意义。
+&gt; 美国再也不敢小瞧我们了。
+- 背景：回答听众关于战争改变大不大的提问，从中国角度总结朝鲜战争奠定强国地位的影响。
+&gt; 他是美国历史上第一次在未取得胜利的情况下签署停战协定的司令官。
+- 背景：引用联合国军最后一任司令官马克·克拉克的自我承认，说明美国对这场战争的定性。
+&gt; 伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家。
+- 背景：总结战争对朝韩双方的伤害，指出三八线悲剧延续至今。
+&gt; 既然海上没办法进行战斗，那就只能在陆地上进行战斗。
+- 背景：解释中国为何选择抗美援朝而非收复台湾，因刚建国缺乏海军实力，只能发挥陆军优势。
 &gt; 长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。
-&gt; 如果朝韩要是统一，大概率应该是韩国兼并朝鲜，毕竟经济影响和综合实力摆在这儿。
+- 背景：说明中国出兵后的战斗意志体现，以两场关键战役作为例证。
 &gt; 俄罗斯和朝鲜都不希望咱们过分强大，然后不想过多依附于我们，所以说在那个图们江出海口给封死了。
-&gt; 韩军贯彻的是以前二战时期昭和日军的那套武士道精神的那种管理体制，老兵欺负新兵，军队的霸凌事件一直蔓延到今天都屡见不鲜。
+- 背景：回答中俄朝关系现状，指出图们江出海口问题至今未解决的原因。
 # Q&amp;A 环节
-**听众**：战争开始和结束时，韩国和朝鲜的势力有很大差别吗？这场战争改变大吗？
-**主讲人**：从中国角度来说，奠定了我们强国的地位，美国再也不敢小瞧我们。1967年越南战争时期，中国警告美国绝对不允许越过北纬十七度线，否则中国必将出兵越南，美国未敢越过。这场战役在美国被称为被遗忘的战争，联合国军最后一任司令官马克·克拉克承认，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
+**听众**：这场战争开始和结束时，韩国和朝鲜的势力差别大吗？战争的改变大吗？
+**主讲人**：从中国角度来说，奠定了强国地位，美国再不敢小瞧我们。1967年越南战争时期，中国警告美国绝对不允许越过北纬十七度线，否则中国必将出兵越南，美国未敢越过。这场战役在美国被称为“被遗忘的战争”，最后一任司令官马克·克拉克承认是美国历史上第一次在未取得胜利的情况下签署停战协定。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
 **听众**：现在越南还分南北吗？
 **主讲人**：没有，越南是统一的。美国最终放弃了南越，北越趁机会把南越统一了。
 **听众**：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
-**主讲人**：当然是韩国更好玩。朝鲜旅游没有人身自由，入境搜手机检查，没有无线网，只有平壤有网络运营商，类似中国八九十年代状态；手机落后很慢，国际漫游和网络非常贵。那几天就是参观主体思想和社会主义辉煌建设成就，类似以前文革时期那种思想，活在异次元世界当中。
+**主讲人**：当然是韩国更好玩。朝鲜旅游没有人身自由，进入境内第一件事就是搜手机检查，没有无线网和网络。只有平壤有自己的网络运营商，类似中国八九十年代的状态，手机很落后很慢，国际漫游和网络非常贵。那几天就是参观主体思想和社会主义辉煌建设成就，类似以前文革时期无产阶级高于一切的思想，活在一种异次元的世界当中。
 **听众**：他们普通人可以上网吗？
-**主讲人**：普通人不能上网，局域网都很有限，连电脑和5G手机都用不起。外部有韩国用韩剧作为意识形态宣传武器，老百姓知道真相后会颠覆政权，所以那么多朝鲜老百姓往韩国跑，鲜有韩国人去朝鲜，这就是脱北者。
-**听众**：他们有拿飞机往朝鲜发传单、发韩国文化那种图吗？
-**主讲人**：有的。朝鲜严防，只要被发现谁家私藏，肯定要被追究连带责任。
+**主讲人**：普通人不能上网，局域网都很有限，普通人连电脑和5G手机都用不起。外部有韩国用韩剧作为意识形态宣传武器，老百姓知道真相后会颠覆政权，所以那么多朝鲜老百姓都往韩国跑，鲜有韩国人去朝鲜，这就是脱北者。
+**听众**：他们有拿飞机往朝鲜发传单，发韩国文化那种图，文化入侵？
+**主讲人**：有的。朝鲜严防，只要被发现谁家私藏传单，肯定要追究连带责任。
 **听众**：朝鲜那边有啥好玩的？
-**主讲人**：也就平壤那边看看志愿军抗美援朝功绩，还有开城，毕竟是朝鲜半岛三千年古都，特产小人参。整个朝鲜半岛都盛产这玩意儿。
-**听众**：朝鲜有他们古代的文化吗？像高丽，还有韩剧里讲的朝鲜古代将军那些。
-**主讲人**：朝鲜半岛文明是伴随中华文明的衍生物，文明有3500年历史，最早是商周时期形成初步文明。高丽半岛一直是中华文化圈中原附属国的形式存在，一直到甲午战争清朝战败，朝鲜才彻底脱离与中国隶属关系，成立大韩帝国，后来与日本合并，二战后复国又被分裂。
-**听众**：朝鲜是不是有像北京或俄罗斯那样很大的广场？平壤的金日成广场，是以领导人命名的吗？
+**主讲人**：也就平壤看看志愿军抗美援朝的功绩，还有开城，毕竟是朝鲜半岛三千年古都，特产小人参。
+**听众**：朝鲜有他们古代的文化吗？高丽，还有韩剧里讲朝鲜古代将军什么的。
+**主讲人**：朝鲜半岛文明是伴随中华文明的衍生物，有3500年历史，最早是商周时期形成初步文明。高丽半岛一直是中华文化圈中原附属国的形式存在，直到甲午战争清朝战败后，朝鲜才彻底脱离与中国的关系，成立大韩帝国，后来跟日本合并，二战之后复国又被分裂。
+**听众**：朝鲜是不是有像北京或俄罗斯那样很大的广场？平壤的金日成广场，是以领导人命名吗？
 **主讲人**：对，以领导人来命名，他们大将军、大元帅这样的。
 **听众**：南北之间的割裂有什么历史渊源？为什么会成为两个政权？
-**主讲人**：一开始美国和苏联都希望在朝鲜半岛建立缓冲区。美国在三八线以南单独建立韩国，是为了保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建立卫星附属国，所以在朝鲜北部宣布北朝鲜独立。最初计划像奥地利那样普选建立统一民选政府，但美苏关系恶化非常快，所扶植的领导人也各有心思，由于意识形态不同，最终建立了两个国家，这也是朝鲜战争爆发的缘由。
+**主讲人**：一开始美国和苏联都希望在朝鲜半岛建立缓冲区。美国分出三八线以南单独建立韩国，是为了保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建立卫星附属国，所以在朝鲜北部宣布北朝鲜独立。最初计划像奥地利那样普选建立统一民选政府，但美苏关系恶化得非常快，所扶植的领导人也各有心思，由于意识形态不同，最终建立了两个国家，这也是朝鲜战争爆发的缘由。
 **听众**：美国没有打败朝鲜，你觉得现在美国对朝鲜的态度是怎样的？
-**主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争时中国出动志愿军帮朝鲜把美国打回去，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南。美国忌惮这一因素，没有主动进攻朝鲜，也没再次挑起武装冲突。朝鲜金家也担心江山被颠覆，不敢贸然发动战争。
-**听众**：现在的朝韩对立可以认为是微妙的平衡吗？如果当时没有冷战布局争夺半岛控制权，大一统的朝鲜半岛会是什么形态？大号朝鲜还是平衡的韩朝？
-**主讲人**：如果朝鲜战争时美国没有下场救援韩国，今日朝鲜可能是苏联卫星国，是牵制中国的一颗钉子，也是威胁美国在亚洲尤其是日本的定时炸弹。现在朝韩若统一，大概率是韩国兼并朝鲜，毕竟经济和综合实力摆在那儿；北方有充足优质兵源及核武器、导弹等尖端武器，统一后对整个东北亚都是不稳定的定时炸弹。当年越南统一后第二年就进攻柬埔寨和泰国，被逼到1979年中国出兵对越南发动自卫反击战，越南尚且如此，朝鲜半岛统一后局势更不可控。
+**主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争时中国出动志愿军帮着朝鲜把美国打回去，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南。美国比较忌惮，没有主动进攻朝鲜，也没有再次挑起朝鲜半岛武装冲突。朝鲜金家也担心贸然发动战争后江山被颠覆，所以也不敢发动战争。
+**听众**：现在的朝韩对立局面，可以认为是韩国和西方国家在背后支撑，是一个微妙的平衡。如果当时没有形成冷战布局、互相争夺半岛控制权的话，大一统的朝鲜半岛会是什么形态？大号的朝鲜还是平衡的韩朝？
+**主讲人**：如果朝鲜战争时美国没有下场救援韩国，今日朝鲜可能是苏联的卫星国，是牵制中国的一颗钉子，也是威胁美国在亚洲尤其是日本的定时炸弹。现在朝韩若统一，大概率是韩国兼并朝鲜，毕竟经济影响和综合实力摆在那儿；北方有充足优质兵源以及核武器和导弹等尖端武器，统一后对整个东北亚地区都是不稳定的定时炸弹。当年越南统一后第二年就进攻柬埔寨和泰国，被中国79年出兵自卫反击，越南尚且如此，朝鲜半岛统一后局势更加不可控。
 **听众**：你感觉现在中国、俄罗斯和朝鲜之间关系怎么样？
-**主讲人**：各怀鬼胎。咱们和朝鲜、俄罗斯的问题主要是图们江出海口问题，到今天还拖着没着落。
+**主讲人**：各怀鬼胎。咱们和朝鲜、俄罗斯的问题，主要就是图们江出海口的那个问题，到现在还拖着没有着落。
 **听众**：什么出海口？
-**主讲人**：图们江是俄罗斯和朝鲜的界江，是日本海的出海口。中朝俄边境那块国际水域航道可以通行，但俄罗斯和朝鲜建了一座小桥，大船没法过去。俄罗斯和朝鲜都不希望咱们过分强大，不想过多依附于我们，所以把图们江出海口封死了。
+**主讲人**：图们江是俄罗斯和朝鲜的界江，那个地方是日本海的出海口，在中朝俄边境那一块。国际水域航道可以通行，但俄罗斯和朝鲜建了一座小桥，大船没法过去。俄罗斯和朝鲜都不希望咱们过分强大，不想过多依附于我们，所以把图们江出海口封死了，都不想把这个出海口让给我们。
 **听众**：朝鲜战争中朝鲜军队和韩国军队有没有发挥什么作用？
-**主讲人**：一开始韩国军队瞎指挥，差点被朝鲜团灭。6月25号战争爆发，7月10号以后南部地面战斗主要是美军和朝鲜人民军打，韩军一开始负责冲人头。差不多1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力。此前韩军对美军有点像猪队友，志愿军跟美军占不到便宜时都从韩军战线突击，美军每一次兵败都是韩军战线崩溃引起。第五次战役中志愿军从朝鲜半岛东部形成反包围突击，把整个韩军前线打崩，美国把韩国第三军团全部撤销。韩军军官主体是二战时期日本人扶植的伪军和傀儡部队骨干，士兵类似国民党抓壮丁强征的农村青年；贯彻昭和日军武士道精神，老兵欺负新兵，军队霸凌事件一直蔓延到今天。
-**听众**：1950年援朝鲜时中国刚成立，实力不是很强，为什么选择抗美援朝而不是收复台湾？
-**主讲人**：台湾和大陆之间海峡距离差不多100公里，中共刚建国没有相应海军实力。1950年朝鲜战争爆发，美国参众两院普遍认为是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。美国越过三八线向中朝边境进发，触动咱们敏感神经，唇亡齿寒深入人心。既然要争取战略主动，解放军陆军很强，海上没办法战斗，就只能在陆地战斗。这也是后来长津湖和上甘岭接连让美军惨败的战斗意志体现，这两场战役到今天也是美国人挥之不去的梦魇。</t>
+**主讲人**：一开始韩军瞎指挥，差点被朝鲜团灭。6月25日朝鲜战争爆发，7月10日以后南部地面战斗主要是美军和朝鲜人民军打，韩军一开始就是冲人头角色。1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力。此前韩军对美军来说像猪队友，志愿军跟美军占不到便宜时都从韩军战线突击，美军每一次兵败都是韩军战线崩溃引起的。第五次战役中志愿军从朝鲜半岛东部反包围突击，把韩军前线打崩，美国把韩国第三军团全部撤销。1952年之前韩军战斗力我不敢恭维，1952年之后还是不可小视。韩军军官主体是二战时期日本人扶植的伪军和傀儡部队骨干，士兵像国民党时期抓壮丁形式强征农村青年，一直贯彻昭和日军武士道精神的管理体制，老兵欺负新兵，军队霸凌事件蔓延至今，是旧日军部队的一种延伸。
+**听众**：1950年援朝时中国刚成立，实力不是很强，为什么选择抗美援朝而不是收复台湾？
+**主讲人**：台湾和大陆之间海峡距离差不多100公里，中共刚建国没有海军实力。1950年朝鲜战争爆发，美国参众两院普遍认为是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，一来防止解放军解放台湾，二来防止国民党反攻大陆。美国后期越过三八线向中朝边境进发，触动了咱们的敏感神经，唇亡齿寒概念深入人心，即便不愿意和美国爆发全面战争，又不得不进行。既然海上没办法战斗，解放军陆军很强，就只能在陆地上战斗。长津湖和上甘岭接连让美军惨败，这两场战役到今天也是美国人挥之不去的梦魇。</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>85.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7464/5672</t>
+          <t>7464/5990</t>
         </is>
       </c>
     </row>
@@ -15694,41 +15541,50 @@
       <c r="C45" t="inlineStr">
         <is>
           <t># 对话概况
-本次为多人闲聊，围绕“出门必带的三样东西”展开，由发言人1起头提问，随后依次讨论钥匙、指甲刀、充电宝、刮胡刀、耳机、工卡等随身物品，并自然延伸到头发打理与个人形象、下雨季节与天气两个话题。发言人2发言最密集，分享个人习惯最多；发言人1、3、4、5各有补充。主要话题包括：出门必带物品、头发打理与个人形象、下雨季节与天气。整体以分享个人习惯为主，未形成明确结论；差异主要体现在随身物品选择上，如发言人2强调多功能指甲刀与刮胡刀，发言人4必带皮圈，发言人5带耳机和工卡，发言人1则因家中指纹锁而不带钥匙。值得记的具体事例：发言人2上班必带三件套为充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，胡子一天能长几毫米；发言人2曾留大胡子被误认为新疆少数民族；发言人3提到李博家地势低，下雨时被淹过。
+这是一场同事间的闲聊，由发言人1发起“出门必带三样东西”的提问开场，随后众人围绕随身物品、头发打理、下雨季节等话题自由漫谈，话题间自然流转。主要话题包括：出门必带物品、头发打理与个人形象、下雨季节与园区积水。以分享为主，未形成明确结论；差异主要体现在个人习惯上，如发言人2强调多功能指甲刀和刮胡刀，发言人1依赖指纹锁不带钥匙，发言人5则必带耳机和工卡。值得记的数字或事例包括：发言人2上班平均每三天带一次刮胡刀，其胡子一天能长几毫米；发言人2曾留大胡子去学校报道被误认为新疆少数民族；发言人3提到李博家因地势低曾被淹。
 # 交流内容
-- **出门必带物品**：发言人1发起「出门必带三样东西」提问，发言人2答`手机`、`充电宝`、`指甲刀`，并说明指甲刀为多功能，可`刮指甲`、`磨手掌`；发言人3答`钥匙`，发言人1表示必须带钥匙，但家中用`指纹锁`无需钥匙；发言人4认为钥匙`破坏性强`，会套起来或挂起来；发言人2称已用`电子锁`多年，没有钥匙概念，以前还把`扣耳勺`挂在钥匙上。
-  - 发言人4：必带`皮圈`绑头发，发言人2追问不带会怎样，发言人4答头发想绑时无法绑；发言人2好奇初中男生爱薅女生头发圈，发言人1表示无此爱好。
-  - 发言人2：上班必带三件套为`充电宝`、`手机`、`刮胡刀`，平均`每三天`带一次刮胡刀，因胡子长得快，`一天能长几毫米`，不带会痒；发言人1建议在家刮，发言人2答有时来不及，用`电动刮胡刀`在单位对着镜子刮。
-  - 发言人5：每天带`手机`、`耳机`和`工卡`；发言人2称耳机和工卡直接放单位，`刷脸`进楼；发言人1补充领`夜宵`需工卡，发言人2称领完即放回工位。
-  - 发言人3：提出带`纸巾`、`伞`；发言人1表示不背包就不带伞，发言人2建议带`一块砖重量`的充电宝，既能充电又能防身。
-- **头发打理与个人形象**：发言人2好奇初中男生薅女生头发圈的原因，并讨论女生绑头发；发言人1认为`散头发比绑好看`，不希望女生绑；发言人2假设自己是女生会披发，显得`脑袋小`；发言人3建议`弄个公分两边补点`。
-  - 发言人2：提到高中时想学`民谣吉他`、留长发大胡子，后因不好打理放弃；尝试过留大胡子，去学校报到时被误认为`新疆少数民族`。
-- **下雨季节与天气**：发言人1称`秋天容易下雨`，发言人2好奇为何不是春天；发言人4认为`北京夏天容易下雨`，发言人1补充`夏春秋`都下雨、夏天多`暴雨`，北京下雨少且`无季节性`。
-  - 发言人3：提到每年下雨`园区门口都是水`，`李博`家地势低、去年被淹过；发言人2建议住`三楼以上`。
+- **出门必带物品**：发言人1起头问「出门必带的三样东西」，发言人2答`手机`、`充电宝`、`指甲刀`，并说明指甲刀为多功能，可`刮指甲`、`磨手掌`；发言人3答`钥匙`，发言人1表示必须带钥匙，但自家门是`指纹锁`，无需钥匙。
+  - 发言人4认为钥匙`破坏性挺强`，会`套起来`或`挂起来`；发言人2称已用`电子锁`多年，没有钥匙概念，用指甲刀平替钥匙，以前还把`扣耳勺`挂在钥匙上。
+  - 发言人4表示一定会带`皮圈`绑头发；发言人2追问不带皮圈会怎样，发言人4答头发想绑时无法绑。
+  - 发言人2称上班必带三件套`充电宝`、`手机`、`刮胡刀`，平均`每三天`带一次刮胡刀，因胡子长得快，`一天能长几毫米`，不带会痒；在家来不及就用单位的`电动刮胡刀`。
+  - 发言人5称每天带`手机`、`耳机`和`工卡`；发言人2说耳机和工卡直接放单位，`刷脸`进门；发言人1提到领`夜宵`需工卡，发言人2领完即把工卡扔回工位。
+  - 发言人2建议带`一块砖重量`的充电宝，既能充电也能防身；发言人1表示不背包就不带伞，发言人3提到出门要带`纸巾`和`伞`。
+- **头发打理与个人形象**：发言人2好奇初中男生喜欢`薅女生头发圈`的原因，自称不理解这个兴趣点；发言人1表示没有此爱好，并认为`绑头发没有散头发好看`。
+  - 发言人2称若自己是女生肯定不绑，绑了显得`脑袋大`，披着显得脑袋小；发言人3建议`弄个公分两边补点小点`，发言人2表示认同。
+  - 发言人2提到高中时想留`长发`和`大胡子`，后因不好打理放弃；曾留大胡子去学校报道，被误认为`新疆少数民族`，发言人3问是否尝试过，发言人2确认尝试过。
+- **下雨季节与园区积水**：发言人1认为`秋天容易下雨`，发言人2好奇为何不是春天，发言人4认为`北京夏天容易下雨`，发言人1称北京下雨`没季节性`，夏天易下`暴雨`。
+  - 发言人3提到每年下雨`园区门口都是水`，`李博`家因`地势低`被淹过；发言人2建议住`三楼以上`，发言人3补充李博家妹子早上送孩子出门。
 # 关键原话
 &gt; 手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。
+- 发言人2回答“出门必带三样东西”时，说明自己带的多功能指甲刀可刮指甲、磨手掌。
+&gt; 对呀，我必须带钥匙，不带钥匙就行。
+- 发言人1回应发言人3“钥匙”的答案，强调自己出门必须带钥匙。
 &gt; 我我已经好多年的电子锁了，我都没什么钥匙的概念了都。然后所以说拿指甲刀来平替钥匙了。
+- 发言人2解释自己因长期使用电子锁，已用指甲刀替代钥匙功能。
 &gt; 对，所以说我上班必带三件套，充电宝、手机、刮胡刀。
+- 发言人2在讨论上班随身物品时，总结自己的上班三件套。
 &gt; 我现在每天就是手机、耳机和工卡。
-&gt; 反正要是我是女的，我肯定不绑。要一绑的话，我自个的角度就觉得显得自己脑袋很大，对不对？
-&gt; 因为初中那会好多男生去薅女生的头发，我不知道他们为什么那喜欢这样，然后我也不太理解这个兴趣点在哪里。
+- 发言人5在讨论上班必带物品时，说明自己每天携带手机、耳机和工卡。
+&gt; 反正要是我是女的，我肯定不绑。要一绑的话，我自个的角度就觉得显得自己脑袋很大。
+- 发言人2在讨论女生绑发与披发时，从自身角度说明若自己是女生会选择披发。
 # 共识与分歧
-- **共识**：**多数人认同“手机必带”**，理由是手机集成了门禁、打卡、支付等功能，且发言人1家为指纹锁、发言人2用电子锁多年，钥匙需求被弱化；同时**普遍认可随身物品应兼顾实用与便利**，如发言人2强调充电宝“既能充电也能防身”，发言人5以手机、耳机、工卡为每日标配。
-- **分歧一（必要 vs 安心）**：钥匙是否必带。发言人1坚持必带钥匙，理由是习惯使然；发言人2因电子锁普及已无钥匙概念，用指甲刀“平替”钥匙；发言人4则因钥匙破坏性强而选择套起来或挂起来——分歧本质是**功能必要性与心理安全感**的差异。
-- **分歧二（审美差异）**：头发绑与不绑。发言人1认为散头发比绑好看，不希望女生绑；发言人2假设自己是女生会披发以显脑袋小；发言人3建议“弄个公分两边补点”——分歧属**个人审美偏好**，无对错。
-- **分歧三（习惯差异）**：上班携带物品。发言人2必带刮胡刀（因胡子长得快，一天几毫米），发言人5带耳机和工卡，发言人1仅带手机——差异源于**个人需求与单位环境**（如刷脸进门、工卡放工位）。
-- **本场倾向**：以分享个人习惯为主，未形成明确结论；讨论中**多数人认可电子锁减少钥匙依赖**，但对“必带”的定义（刚需 vs 备用）未达成一致。
+- **共识**：**手机是出门必带的核心物品**，多数人默认手机不可或缺，分歧仅在“必要”与“安心”之间——有人强调手机可替代门禁、打卡等功能，有人则将其视为习惯性随身物。
+- **分歧一（习惯差异）**：钥匙是否必带。发言人1坚持带钥匙，但家门为指纹锁，实际用不上；发言人2已用电子锁多年，认为指甲刀可“平替”钥匙。分歧源于居住条件与使用习惯不同，而非必要性之争。
+- **分歧二（审美差异）**：长发绑起还是披散。发言人1认为散头发更好看，发言人2从“显脑袋小”角度主张披发，发言人3则建议“弄个公分两边补点小点”。分歧属个人审美偏好，无对错。
+- **分歧三（经验差异）**：下雨季节认知不一。发言人1认为秋天易下雨，发言人4认为北京夏天多雨，发言人1又补充北京下雨“没季节性”。分歧源于各自生活经验与观察角度不同，未形成统一结论。
+- **本场倾向**：以分享个人习惯为主，未形成明确共识或决策；讨论多由发言人2的好奇心驱动（如初中男生薅头发圈、秋天为何多雨），多数人随兴回应，未深入论证。
 # 延伸话题与后续
-- **字节员工不录出来会有什么惩罚**：发言人2问及字节员工若不录出来会怎样，发言人5回应「有点小的惩罚吧」，发言人2追问具体惩罚，发言人5表示「那就得问他们了」，话题未获明确答案即被发言人1以「不知道啊」带过，未继续深究。
-- **为什么秋天容易下雨**：发言人1提到秋天容易下雨，发言人2好奇为何不是通常认为的春天多雨，发言人4提出北京夏天易下雨，发言人1补充夏春秋都有雨、夏天多暴雨，发言人3未听清问题，话题未形成定论即被发言人4以「时间差不多了，我们先停吧」结束。</t>
+- **字节员工不录出来的惩罚**：发言人1提到“字节员工哦，要录出来”，发言人2追问“他们如果不录出来会怎么样呢”，发言人5回应“有点小的惩罚吧”，发言人2再问“比如说什么样的惩罚”，发言人5答“那就得问他们了”，发言人2评价“那这不成了剥削员工了吗”。该话题未获明确解答，讨论即止。
+- **初中男生薅女生头发圈的原因**：发言人2提出“为什么初中很多男生喜欢薅女生的后边那个头发圈啥的”，发言人1表示“我没有特别爱好”，发言人2自述“我也不太理解这个兴趣点在哪里”，话题未展开即转入头发打理讨论。
+- **秋天为何容易下雨**：发言人1称“包里有秋天就容易下雨呀”，发言人2追问“为什么说秋天容易下雨？这挺好奇的”，发言人4提出“北京是夏天容易下雨”，发言人1回应“北京倒是下雨很少，也没个季节性”，未形成定论。</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3851/2247</t>
+          <t>3851/2415</t>
         </is>
       </c>
     </row>
@@ -15925,62 +15781,67 @@
       <c r="C46" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议为多人闲聊式交流，共5位发言人（编号1至5）参与，围绕手机常用APP、AI助手、视频平台、音乐APP、听歌场景及歌手偏好等话题展开。讨论由发言人1提议「说手机里最常用的三个APP」开场，随后自然延伸至AI助手、视频与音乐平台等日常数字生活议题。各发言人依次分享个人使用习惯与偏好，以分享观点为主，未形成统一结论。关键锚点包括：**5位**发言人、**6个**议题板块（手机常用APP、AI助手、视频平台、音乐APP、听歌场景、歌手偏好）、专名**Taylor Swift（梅梅）**。讨论按议题逐块推进，由主持人式提问引导，各成员轮流发言，整体呈漫谈发散态势，未涉及正式决策或行动项。
+本次为5人（发言人1至发言人5）参与的漫谈式闲聊，围绕手机常用APP、AI助手与浏览器、视频与音乐平台、歌手喜好等话题展开，各成员分享个人偏好，以分享观点为主，未形成统一结论。讨论由「手机里最常用的三个APP」起头，随后自然发散至AI助手使用习惯、视频平台付费与广告、音乐APP适配与听歌场景、歌手与乐队喜好等议题。关键锚点包括：发言人2自述停留在「浏览器加纸质地图、尺子、圆规和铅笔标注」的思维模式；发言人5提到「单框架手机」导致网易云不适配、需用「卓翼通」；发言人2提及Taylor Swift（梅梅）因绯闻消沉后重新走红。讨论整体按议题逐块推进，各成员轮流发言，穿插英文表达与玩笑，未涉及正式决策或行动项。
 # 发言要点
 ## 手机常用APP
-- **发言人2**：最常用知乎、小红书、谷歌。
-- **发言人3**：最常用微信、抖音、淘宝、京东等购物平台。
-- **发言人4**：最常用微信、小红书。
-- **发言人5**：认为微信使用普遍，大家应该都用。
-## AI助手使用情况
-- **发言人4**：用手机自带的小布小布，已不用浏览器，直接搜小布小布。
-- **发言人5**：认为小布小布就是豆包。
-- **发言人3**：也下载了豆包，认为AI小助手回答更精准、总结性强、更全面。
-- **发言人1**：下载了百度千问、吉米等多个AI应用。
-- **发言人2**：仍停留在浏览器加纸质地图、尺子圆规铅笔标注的思维模式，不确定AI回答是否正确，自认比大家落后一代。
-## 视频平台使用情况
-- **发言人5**：b站和YouTube用得比较多，希望中英混杂内容能被识别。
-- **发言人4**：指出YouTube手机一般翻不了墙；单框架手机现在连YouTube都下不了了。
+- **发言人2**：最常用知乎、小红书、谷歌三个APP。
+- **发言人3**：主要用微信、抖音、淘宝、京东等购物与短视频平台。
+- **发言人4**：常用微信和小红书，并提到手机上有小布小布，现在都不用浏览器了，直接搜小布小布。
+- **发言人5**：认为微信感觉大家都用，应该挺多的。
+## AI助手与浏览器使用
+- **发言人4**：用手机上的小布小布直接搜索，不再用浏览器。
+- **发言人5**：认为小布小布就是豆包；**发言人3**：自己也下载了豆包。
+- **发言人1**：提到自己装了百度千问、吉米等多个AI应用。
+- **发言人3**：补充提到重庆元宝；**发言人1**：表示没有元宝。
+- **发言人2**：表示仍停留在浏览器加地图测绘、用尺子圆规铅笔标注的思维模式，不太喜欢用AI软件，因为不确定它说的是否是对的，感觉比大家落后了一代。
+- **发言人3**：认为AI小助手更全面、回答更精准、总结性比较强。
+- **发言人1**：反问「你能判断他说的是对的吗」，对AI回答的准确性提出质疑。
+## 视频平台与播放器
+- **发言人5**：B站用得比较多，也常用YouTube，希望中英混杂的内容能被识别。
+- **发言人4**：指出YouTube手机一般翻不了墙；**发言人5**：补充单框架手机现在连YouTube都下不了了。
 - **发言人1**：发现国内付费电视剧在YouTube上不要钱。
-- **发言人2**：认为YouTube上好多内容也得付费，反而一些小网站不用花钱；平台大有版权纠纷所以需付费，小网站没有版权纠纷。
-- **发言人3**：常用腾讯视频、爱奇艺、优酷、芒果TV，会点进去看有没有想看的。
-- **发言人2**：因广告时间太长等不起，改用b站直接看。
-## 音乐APP使用情况
-- **发言人5**：用网易云较多；单框架手机网易云不适配，现在全用卓翼通。
-- **发言人2**：以前用酷狗、酷我；提到欧美音乐平台虾扎，认为其有更多欧美演唱会版本，国内网易音乐相对较少。
-- **发言人1**：认为苹果music唱的多是小众歌手。
-- **发言人2**：解释虾扎小众翻唱多，大牌因版权纠纷播不出来。
-## 听音乐场景与偏好
-- **发言人1**：上班时候听音乐。
-- **发言人4**：通勤路上听，要戴降噪耳机。
-- **发言人2**：随时都可能听；在柏林坐地铁时听音乐代入感强，因为地铁比较安静。
-- **发言人3**：询问是否真实听到音乐内容还是随便放；发言人2回应当然要听内容，否则没意义。
-- **发言人4**：补充也有人听音乐就是听旋律，甚至听纯音乐。
-## 喜欢的歌手与乐队
-- **发言人3**：最近刷到谢霆锋演Taylor Swift，喜欢谢霆锋，提到《玉蝴蝶》等九十年代作品。
-- **发言人1**：认为五月天以前挺好，新发的还行但唱不上去了。
-- **发言人2**：疑惑梅梅（Taylor Swift）为何重新火起来——中学时（2010年代开头）已很火，后因绯闻消沉，最近又火，对九零后和零零后影响都很深。
-- **发言人3**：认为梅梅演唱有感染力，虽然听不懂但氛围特别好。
-- **发言人2**：提到梅梅与猫头鹰之城主角亚当·杨传过绯闻，当时从东南卫视台湾节目看到。
-- **发言人4**：承认梅梅全球影响力大。
+- **发言人2**：指出YouTube上好多内容也得付费，反而一些小网站不用花钱；因为平台比较大会有版权纠纷，所以需要付费。
+- **发言人3**：提到经常用到腾讯视频、爱奇艺、优酷、芒果TV等播放器APP。
+- **发言人2**：抱怨广告时间太长，不愿意等，用B站直接看。
+- **发言人3**：提到现在很多电视剧可以看广告获得VIP时长。
+- **发言人5**：认为APP太多了，都不知道开哪个VIP。
+## 音乐APP与听歌习惯
+- **发言人4**：询问大家音乐APP用QQ还是什么；**发言人5**：网易云用得比较多。
+- **发言人2**：以前用酷狗、酷我多一些。
+- **发言人5**：提到单框架手机网易云一直不适配，现在网易云全用卓翼通，其他都适配了。
+- **发言人2**：提到欧美音乐平台虾扎，认为那边欧美国家演唱会版本更多，相比国内网易音乐；但小众翻唱多，大牌有版权纠纷播不出来。
+- **发言人1**：提到苹果Music；认为虾扎唱的都是小众歌手。
+- **发言人3**：询问大家大概什么时候听音乐；**发言人1**：上班时候听；**发言人4**：通勤路上听；**发言人2**：说不准什么时候都有。
+- **发言人2**：认为在柏林坐地铁时听音乐代入感挺好，因为地铁比较安静，听听音乐看看景儿。
+- **发言人3**：追问是真实听到音乐内容还是随便放；**发言人2**：表示当然要听真实内容，否则意义何在。
+- **发言人4**：指出也有人听音乐就是听旋律，甚至听纯音乐的。
+## 歌手与乐队喜好
+- **发言人2**：询问大家最喜欢哪个乐队或歌手组合。
+- **发言人3**：最近刷到谢霆锋演Taylor Swift，喜欢谢霆锋，提到《玉蝴蝶》等老歌，记不清具体年份。
+- **发言人2**：询问大家对五月天和周杰伦那个时期作品的看法；**发言人1**：认为五月天以前挺好，新发的也还行，但唱不上去了。
+- **发言人2**：疑惑梅梅（Taylor Swift）为什么重新火起来——中学时（2010年代开头）她就很火，后来因绯闻消沉很长一段时间，最近又重新火，对九零后和零零后影响都很深。
+- **发言人3**：认为梅梅演唱特别有感染力，虽然听不懂但氛围特别好。
+- **发言人2**：提到Taylor Swift的《Speak Now》《Back To December》《Love Story》等歌，以及梅梅与猫头鹰之城主角亚当杨传出过绯闻，当时东南卫视和台湾节目讲过这一期。
+- **发言人4**：表示对这段绯闻没有很关注，但认为梅梅的确有全球影响力。
 # 共识形成
-- **一致意见**：与会者普遍认可微信为高频常用APP，发言人5指出“微信感觉大家都用”，发言人3、发言人4均将其列入最常用应用；对AI助手“回答更精准、总结性更强”的优势，发言人3明确肯定，发言人1、发言人4、发言人5亦在行动上体现对AI助手的接受（分别使用百度千问、小布小布、豆包）。
-- **主要分歧**：发言人2与其余成员在AI工具信任度上明显不一致——发言人2自述“不太确定它是否说的是对的”，仍停留在“浏览器加地图测绘，用尺子标识”的思维模式，以“大家在用GPS，我还在用纸质地图”作比；发言人1则反问“你能判断他说的是对的吗”，对AI准确性提出质疑，而发言人3、发言人4、发言人5未回应此疑虑。
-- **倾向性认识**：视频平台方面，多数人认同大平台因版权纠纷需付费、广告冗长，发言人2因此改用b站，发言人3则通过“看广告获得VIP时长”应对；音乐平台方面，发言人5指出单框架手机网易云不适配、需用卓翼通，发言人2补充虾扎平台拥有更多欧美演唱会版本，但发言人1认为其“唱的都是小众歌手”，双方对平台内容定位存在不同评价。
+- **一致意见**：多数成员认可AI助手比浏览器更全面、回答更精准、总结性更强（发言人3），且微信、小红书、抖音等社交与内容类APP使用普遍（发言人5认为微信大家都用）；视频平台广告时间过长，**B站直接观看成为规避广告的替代选择**（发言人2）。
+- **倾向性认识**：在AI工具接受度上，发言人2明确表示仍停留在浏览器、纸质地图、尺子、圆规、铅笔标注的思维模式，不确定AI回答是否正确，与发言人4、发言人3、发言人1使用小布小布、豆包、百度千问等AI助手的做法形成代际差异；在音乐平台选择上，发言人5用网易云较多，发言人2以前用酷狗、酷我，并提到欧美平台虾扎有更多欧美演唱会版本，但发言人1认为虾扎唱的都是小众歌手，发言人2补充称大牌有版权纠纷播不出来。
+- **主要分歧点**：关于YouTube，发言人1发现国内付费电视剧在YouTube免费，发言人2指出YouTube上很多内容也要付费，但一些小网站免费，且平台大有版权纠纷需付费；关于梅梅（Taylor Swift）重新走红，发言人2疑惑其因绯闻消沉后为何再度火爆，发言人3认为其演唱会有感染力、氛围好，发言人4表示未关注相关绯闻。
 # 待探讨问题与后续
-- **未确认**：发言人2对AI助手回答的准确性存疑，表示不确定其说法是否正确，因此仍停留在浏览器、纸质地图、尺子、圆规和铅笔标注的思维模式，未转向AI工具。
-- **未确认**：发言人2疑惑梅梅（Taylor Swift）为何在沉寂一段时间后重新火起来，并提及她中学时期（约2010年代）已走红、后因绯闻消沉，但未就重新走红原因得出定论。
-- **待核实**：发言人5提到单框架手机无法下载YouTube，且网易云音乐在该类手机上不适配、需用卓翼通替代，但未进一步核实该技术限制的具体原因或普遍性。
-- **未定论**：关于YouTube上国内付费电视剧免费观看的现象，发言人1与发言人2看法不一——发言人1认为YouTube上免费，发言人2则认为很多内容仍需付费、反而一些小网站不用花钱，双方未达成一致。
-- **未定论**：发言人2提到欧美音乐平台虾扎有更多演唱会版本，发言人1则认为苹果音乐以小众歌手为主，对平台内容优势的比较未形成统一认识。</t>
+- **未确认**：发言人2对梅梅（Taylor Swift）中学时期走红、因绯闻消沉、近期重新火起来的判断，以及她与猫头鹰之城主角亚当杨的绯闻，发言人4表示「没有很关注」，该说法未获其他成员印证。
+- **未定论**：发言人2质疑梅梅为何重新火起来，发言人3认为其演唱会有感染力、氛围好，但未解释重新走红的具体原因，话题未深入即被时间打断。
+- **待核实**：发言人5提到单框架手机下不了YouTube、网易云不适配需用卓翼通，发言人4指出手机翻不了墙，相关技术限制未展开核实。
+- **未确认**：发言人1发现国内付费电视剧在YouTube上免费，发言人2指出YouTube上很多内容也要付费、但一些小网站免费，免费与付费的具体范围未厘清。
+- **未定论**：发言人2表示不确定AI软件回答是否正确，仍停留在浏览器、纸质地图、尺子、圆规、铅笔标注的思维模式，与其他人使用AI助手的偏好形成分歧，未进一步讨论。
+- **未提及**：原文未涉及分工或后续约定。</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>42.5</v>
+        <v>48.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4259/2479</t>
+          <t>4259/2998</t>
         </is>
       </c>
     </row>
@@ -16157,70 +16018,65 @@
       <c r="C47" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论由**发言人1**主持，围绕**2022年俄乌战争中俄军表现**展开，对比游戏与媒体中的俄军形象，分析俄军战斗力、后勤指挥问题及乌克兰地缘重要性，并延伸至俄罗斯文化、旅游与历史。讨论面向对俄乌战争、俄军实力及俄罗斯地缘政治感兴趣的参与者，以自由发言形式进行。
-核心判断包括：**俄军单兵素质厉害，但后勤和指挥拉垮**，被形容为“矮脚巨人”或“柯基”；战争从闪电战变为持久战，双方重装备耗光后“从钢铁洪流变成菜鸡互啄”；乌克兰在欧洲认知中被称为“**欧洲之门**”，欧洲自发达支援乌克兰以将俄罗斯挡在亚洲之外。关键锚点包括：**2022年**俄乌战争爆发、基辅攻防战、**《红警》《战地风云》**等游戏中的俄军形象、**东宫**（世界四大艺术博物馆之一）。
-对听众而言，本讨论有助于理解俄乌战争的实际战况与媒体/游戏刻画的差异，以及乌克兰在欧洲地缘格局中的关键地位。
+本次讨论由发言人1主持，围绕2022年俄乌战争中俄军的实际表现展开，对比游戏与影视中的俄军形象，并延伸至俄罗斯的历史、文化及欧洲对俄认知。发言人1指出，战争爆发前全世界预期俄军将迅速占领基辅，但泽连斯基扛住进攻并将俄军打回白俄罗斯与乌克兰边境；俄军基层官兵误以为演习，进入乌克兰后遭遇民兵自发抵抗，战争从闪电战转为持久战。与会者普遍认为，俄军单兵素质强，但总体表现拉垮，主要问题在后勤与指挥；发言人4补充，俄军主动进攻表现不佳，但防守反击时能迸发战斗力。发言人1用“矮脚巨人”形容俄军，并引用名画《伏尔加河的船夫》作比。双方重装备耗光后，战场退化为隔战壕扔手雷、无人机互炸，从“钢铁洪流”变成“菜鸡互啄”；俄罗斯无人机依赖伊朗供应，乌克兰则靠北约持续输血。关于游戏中的俄军形象，发言人2、4认为游戏多由西方主导，将苏联/俄罗斯塑造为反面、凶猛、研究邪乎武器的形象，如《红警》将共产主义解放思想抹黑为“心灵控制器”。发言人3表示对俄军无直观印象。
+发言人1阐述乌克兰对俄罗斯的立国意义，称欧洲将乌克兰视为“欧洲之门”，将俄罗斯人视为“亚洲野蛮人”“半兽人”，因其曾被蒙古人统治二百年而不被欧洲接纳；欧洲支援乌克兰是为将俄罗斯挡在亚洲之外，防止其握紧乌克兰后欧洲再次生活在阴影之下。发言人1分享俄罗斯旅游经历，推荐圣彼得堡东宫、克里姆林宫、红场，称东宫为世界四大艺术博物馆之一，连续三次未逛完；藏品来源包括殖民掠夺、王室联姻赠送、二战从德国运回等，涵盖欧洲、中东、东亚、中亚、北非等地。俄罗斯以俄罗斯族为主，东扩类似美国西进运动。
 # 核心观点与论证
-## 论点：俄军在俄乌战争中的表现与预期严重不符
-- **战争预期**：2022年俄乌战争爆发时，全世界认为战争天平会向俄罗斯一边倒，基辅会很快被占领，乌克兰会被消灭，泽连斯基会流亡。
-- **实际战况**：泽连斯基不但扛住俄罗斯进攻，反而把俄军从基辅打回白俄罗斯和乌克兰边境，战争从闪电战变成持久战。
-- **基层不知情**：俄军基层官兵不知道2022年会进攻乌克兰，好多部队收到命令以为是去演习，结果演着演着就进了乌克兰。
-- **遭遇民兵抵抗**：第一批部队进入乌克兰时遭遇的是民兵自发抵抗，而非军队有组织的进攻，一来二去从闪电战变成持久战。
-- **情报经费贪污**：普京底下的情报官员把用于策反乌克兰官员的经费全部贪污瓜分，没想到普京真的会进攻乌克兰，结果乌克兰高官没收到策反经费。
-- **克里米亚耻辱**：2014年俄罗斯占领克里米亚后，乌克兰上下迸发出民族仇恨，类似九一八事变一枪不发丢掉整个克里米亚的耻辱感，当权者的无能与腐败令民众不满。
-- **腐败问题**：发言人3提到俄军腐败，涉及国防部长「特别会盖房子」，发言人1补充称其为「总包工头」。
-- **防守反击特点**：发言人4认为俄罗斯打仗得被打到家破国亡才能迸发战斗力，打防反行，主动进攻感觉不行。
-- **单兵强整体弱**：俄军单兵素质很厉害，但总体拉垮，主要在后勤和指挥上，像「矮脚巨人」或柯基——腿特别短，支撑不起庞大身子。
-- **战场形态退化**：双方把重装备都耗光了，只能隔着战壕互相扔手雷或互相用无人机互炸，从钢铁洪流变成「菜鸡互啄」。
-- **装备来源**：俄罗斯的无人机靠伊朗提供，乌克兰由北约持续输血，类似越战形式——乌克兰相当于北约，俄罗斯相当于越战时期的美国。
-- **战场细节**：乌克兰有人拿细线挂在树上防无人机，无人机飞过去被线刮住，利用惯性冲击力勒住关节部位使其散架。
-## 论点：游戏与媒体中的俄军形象与现实存在巨大反差
-- **游戏形象**：在《战地风云》《使命召唤》《红警》等游戏中，俄军或苏联红军形象与现实中俄军表现有360度反差。
-- **红警创作意图**：发言人2认为红警是美国做出来黑苏联的，发言人4补充称抹黑得很肌肉。
-- **西方主导塑造**：发言人4指出这些游戏大多数由西方主导，苏联形象都是反面的、很猛很变态，研究非常邪乎的武器，规模非常夸张。
-- **具体游戏元素**：发言人1举例《尤里的复仇》中心灵控制器，发言人4提到把人基因改变，发言人3提到生化反应。
-- **意识形态抹黑**：共产主义解放世界的思想被抹黑成心灵控制器，毛子被形容成暴力美学的形象代言。
-## 论点：乌克兰的地缘政治地位与欧洲认知
-- **欧洲之门**：乌克兰在欧洲人的认知里被称为「欧洲之门」，欧洲人认为欧亚分界线在乌克兰，而非乌拉尔山脉和高加索山脉。
-- **地理原因**：白俄罗斯大部分是沼泽地，没法有大规模的运输通道走廊，所以欧洲和亚洲的边界在欧洲人认为始终在乌克兰这一块过渡的地方。
-- **半兽人印象**：俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳，被当成长着欧洲人面孔的亚洲游牧民族，类似冰封王座里贝加尔湖的半兽人反派角色。
-- **欧洲支援动机**：欧洲自发达支援乌克兰，要把俄罗斯挡在亚洲之外，不让它涉足欧洲，因为如果俄罗斯握紧乌克兰，欧洲会再一次生活在曾经的阴影之下。
-- **立国资本**：俄罗斯立国靠乌克兰成为立国资本，没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家，不被欧洲待见。
-- **唇亡齿寒**：欧洲把乌克兰看得很重，明白唇亡齿寒的道理，这也是乌克兰死活不能向俄罗斯妥协的根本原因。
-- **东欧敌视态度**：在美国人认知中俄罗斯既不是朋友也不是敌人，但在欧洲国家尤其是东欧国家——波兰、乌克兰、波罗的海三国——俄罗斯就是敌人、蛮子、半兽人。
-## 论点：俄罗斯的文化、旅游与历史印象
-- **旅游签证影响**：发言人1去过俄罗斯多次，在美国边境入口被拦下，被问去俄罗斯干嘛，差点被怀疑是间谍；发言人2提到去俄罗斯后办美签可能被拒。
-- **东宫推荐**：东宫是世界四大艺术博物馆之一，发言人1连续去三次、每次不同区域都没逛完，圣彼得堡的夏天不错。
-- **藏品来源**：东宫藏品来源包括列强殖民战争掠夺、王室联姻赠送、二战后打进德国运回纳粹产品，以及探险队名义从世界各地获取。
-- **藏品地域范围**：往欧洲深入到德国、法国、荷兰；往东有朝鲜半岛、蒙古、西藏、西夏王陵、敦煌；往南有阿富汗、中亚、埃及、北非、奥斯曼帝国、土耳其。
-- **中亚属地**：中亚斯坦国家以前是俄罗斯属地，乌兹别克斯坦塔什干是重要的一带一路丝绸之路走廊和文明之都，也有不少产品在东宫。
-- **民族构成**：俄罗斯境内有多个共和国，但总的来说以俄罗斯族为主，俄国东扩像美国西进似的源源不断淘金移民。
+## 论点：俄军实际表现与外界预期形成强烈反差
+- **战前预期**：2022年俄乌战争爆发时，全世界预期战争天平向俄罗斯一边倒，基辅会很快被占领，乌克兰会被消灭，泽连斯基会流亡。
+- **实际战况**：泽连斯基扛住俄罗斯进攻，反而把俄军从基辅打回白俄罗斯和乌克兰边境，剧情超出各方反转和认知。
+- **基层不知情**：俄军基层官兵不知道2022年会进攻乌克兰，许多部队收到命令还以为是去演习，结果演着演着就进入乌克兰，第一批部队遭遇的是民兵自发抵抗而非军队有组织进攻。
+- **战争形态转变**：一来二去，俄军从闪电战变成持久战，与《战地风云》《使命召唤》《红警》等游戏里接触到的俄军或苏联红军形象有360度改变。
+## 论点：俄军单兵素质强但总体拉垮，问题在后勤与指挥
+- **单兵与整体反差**：发言人1总结俄军单兵素质很厉害，但总体很拉垮，主要问题在后勤和指挥上，用「矮脚巨人」形容——腿特别短，支撑不起庞大身子，类似柯基的感觉。
+- **防守反击特点**：发言人4认为俄罗斯打仗得被打到要家破国亡时才能迸发战斗力，打防反行，主动进攻感觉一坨。
+- **战场退化**：双方把重装备都耗光了，只能隔着战壕互相扔手雷或无人机互炸，从钢铁洪流变成菜鸡互啄；发言人4认为俄乌战场跟二战时没啥进步，多了点无人机，还是扔手雷，不太先进。
+- **装备依赖**：俄罗斯的无人机靠伊朗提供，乌克兰由北约持续输血，类似越战形式——乌克兰相当于北约，俄罗斯相当于越战时期的美国。
+## 论点：俄军腐败与信息茧房导致战前准备失效
+- **情报经费被贪污**：普京底下的情报官员把用于策反乌克兰官员的经费全部贪污瓜分，没想到普京真的会进攻乌克兰，结果乌克兰高官没收到策反经费。
+- **乌克兰民族情绪**：2014年俄罗斯占领克里米亚后，乌克兰上下迸发出民族仇恨，类似九一八事变一枪不发丢掉整个克里米亚的耻辱感，当权者的无能腐败引发民众不满。
+- **普京决策环境**：发言人1认为普京飘了，活在自己的信息茧房里，对战场真实情况缺乏准确判断。
+## 论点：游戏与影视中的俄军形象是西方主导的抹黑
+- **游戏形象**：《红警》是美国做出来黑苏联的，游戏大多由西方主导，苏联形象都是反面、很猛、很变态，研究非常邪乎的武器，规模非常夸张。
+- **意识形态抹黑**：游戏把共产主义解放世界的思想抹黑成心灵控制器，把毛子形容成暴力美学的形象代言。
+- **具体案例**：发言人1举例《红警》里的尤里的复仇、心灵控制器，以及把人基因改变、生化反应等设定。
+## 论点：欧洲将乌克兰视为欧洲之门，将俄罗斯视为亚洲野蛮人
+- **乌克兰的战略地位**：乌克兰在欧洲人认知里被称为欧洲之门；欧洲人认为欧亚分界线在乌克兰，因为白俄罗斯大部分是沼泽地，没有大规模运输通道走廊。
+- **俄罗斯被排斥**：俄罗斯人被蒙古人统治过二百年，不被欧洲人认可接纳，被当成长着欧洲人面孔的亚洲游牧民族，类似冰封王座里半兽人的反派角色。
+- **欧洲支援动机**：欧洲自发支援乌克兰，不让俄罗斯打赢，因为如果俄罗斯握紧乌克兰，欧洲会再一次生活在曾经的阴影之下；唇亡齿寒的道理欧洲人也明白。
+- **俄罗斯立国依赖**：乌克兰军队前身是苏联红军重要组成部分，俄罗斯立国靠乌克兰成为立国资本；没有乌克兰的俄罗斯帝国终究沦为边缘亚洲国家，不被欧洲待见。
+## 论点：俄军在其他战场的战斗力表现
+- **地方武装战力**：发言人4认为车臣、格鲁吉亚、瓦格纳雇佣兵、库尔德武装等战斗力强，怎么干都干不赢；发言人1补充瓦格纳部队在也门介入内战时战斗力也很猛。
+- **传统大国对比**：发言人4认为美国打地面战也不行，国外传统意义的仗打得都一般。
 # 金句总结
-&gt; 泽连斯基不但扛住了俄罗斯的进攻，反而还把俄军从基辅打回了白俄罗斯和乌克兰的边境。
-&gt; 俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，矮脚巨人的感觉，有点像柯基，腿特别短，支撑不起庞大的身子。
-&gt; 从钢铁洪流变成了最后的菜鸡互啄。
-&gt; 没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。
-&gt; 欧洲的边界是在乌克兰，一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。
-&gt; 俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳，终究被当成是长着欧洲人面孔的亚洲游牧民族。
+&gt; “从钢铁洪流变成了最后的菜鸡互啄。”
+&gt; 背景：发言人1总结俄乌双方重装备耗光后，战场退化为隔战壕扔手雷、无人机互炸的现状。
+&gt; “俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上。”
+&gt; 背景：发言人1回应与会者对俄军表现的讨论，用“矮脚巨人”比喻俄军腿短撑不起庞大身躯。
+&gt; “没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。”
+&gt; 背景：发言人1阐述乌克兰对俄罗斯的立国意义，解释俄乌冲突的历史根源。
+&gt; “欧洲的边界是在乌克兰，所以说一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。”
+&gt; 背景：发言人1解释欧洲持续支援乌克兰、不让俄罗斯打赢的根本原因。
+&gt; “俄罗斯人就是长着欧洲人面孔的亚洲游牧民族。”
+&gt; 背景：发言人1说明欧洲人因俄罗斯曾被蒙古人统治二百年而不接纳其欧洲身份。
+&gt; “毕竟俄罗斯的无人机都是靠伊朗给他的。”
+&gt; 背景：发言人1回应俄乌战场技术水平的讨论，指出俄罗斯在无人机供应上依赖伊朗。
 # Q&amp;A 环节
-**发言人4**：俄罗斯打仗是不是得被打到快家破国亡才能迸发出战斗力，打防守反击行，主动进攻感觉不行？
-**发言人1**：只能说是普京飘了，活在自己的信息茧房里。情报官员把策反乌克兰官员的经费全部贪污瓜分，没想到普京真会进攻乌克兰；加上2014年丢掉克里米亚像九一八事变一样耻辱，乌克兰上下对政府无能与腐败非常不满。基层官兵也不知道要进攻，收到命令还以为是演习，结果第一批部队进乌克兰遭遇的是民兵自发抵抗，一来二去从闪电战变成持久战。
-**发言人4**：游戏里苏联形象都是西方主导塑造的，都是反面、很猛很变态，研究邪乎武器、规模非常夸张。
-**发言人1**：比如红警里的心灵控制器，把共产主义解放世界的思想抹黑成心灵控制器，把毛子形容成暴力美学代言人。
-**发言人4**：感觉俄乌战场打的跟二战时没啥进步，多了点无人机，还是扔手雷，不太先进。
-**发言人1**：双方把重装备都耗光了，只能隔着战壕互相扔手雷或无人机互炸，从钢铁洪流变成菜鸡互啄。俄罗斯无人机靠伊朗提供，乌克兰靠北约持续输血，类似越战形式——乌克兰相当于北约，俄罗斯相当于越战时的美国。
-**发言人2**：去俄罗斯旅游后办美签会不会被拒？
-**发言人1**：上次我去美国，因为去过好几次俄罗斯，在边境入口被拦下，问我去俄罗斯干嘛，我瞎掰扯，差点被怀疑是间谍。美国入境对咱们卡得严。在欧洲国家尤其是东欧，波兰、乌克兰、波利海三国，俄罗斯就是敌人、蛮子、半兽人。
-**发言人4**：俄罗斯东西部差异大不大？远东地区和欧洲那头风格差别很大吧？
-**发言人1**：总的来说还是以俄罗斯族为主，俄国东扩像美国西进似的，源源不断淘金移民。</t>
+**发言人4**：俄罗斯打仗是不是得被打到要家破国亡才能迸发战斗力，主动进攻感觉不行，打防反才行？
+**发言人1**：只能说是普京飘了，活在自己的信息茧房里。情报官员把策反乌克兰官员的经费贪污瓜分，没想到普京真会进攻乌克兰；加上2014年丢掉克里米亚的耻辱，乌克兰上下对政府无能与腐败非常不满。俄军基层官兵也不知道要进攻，以为是演习，结果遭遇民兵自发抵抗，从闪电战变成持久战。
+**发言人4**：感觉俄乌战场跟二战时没啥进步，多了点无人机，还是扔手雷，不太先进。
+**发言人1**：双方重装备都耗光了，只能隔着战壕扔手雷或无人机互炸，从钢铁洪流变成菜鸡互啄。俄罗斯无人机靠伊朗提供，乌克兰靠北约持续输血，类似越战形式。
+**发言人2**：去俄罗斯旅游可以，但出俄罗斯后办美签会被拒。
+**发言人1**：我去美国时因去过几次俄罗斯，在边境被拦下盘问去俄罗斯干嘛，差点被怀疑是间谍。在美国人认知中俄罗斯是普通国家，但在东欧国家尤其是波兰、乌克兰、波罗的海三国，俄罗斯就是敌人、蛮子、半兽人。
+**发言人4**：俄罗斯地域那么宽阔，远东地区和欧洲那头风格差别大吗？
+**发言人1**：总的来说还是以俄罗斯族为主，俄国东扩也像美国西进运动似的，源源不断淘金移民。</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>52.3</v>
+        <v>55.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6103/3392</t>
+          <t>6103/3221</t>
         </is>
       </c>
     </row>
@@ -16323,56 +16179,52 @@
       <c r="C48" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论由贝姐主持，围绕热播电影《南京照相馆》展开，参会成员（发言人2、3、4、5）先各自分享观影印象，随后贝姐系统介绍南京大屠杀的历史背景，并辨析影片中虚构与真实的细节。讨论面向对这段历史感兴趣、希望通过电影切入历史认知的普通观众，整体氛围偏沉重但带有科普性质。
-讨论主要覆盖四个板块：**观影印象**、**历史背景**、**虚构与真实辨析**、**相关纪念馆参观与公众关注度**。贝姐的核心判断有三：其一，电影中主要人物为虚构，但照片拍摄是真实的，真实历史为两名美国传教士拍摄日军暴行，中国照片冲洗人员偷偷拷贝后于战后递交国民政府军事法庭作为审判战犯证据；其二，日军南京大屠杀的深层原因包括自九一八事变以来未遭成规模抵抗的轻敌心态、上海遭遇迎头痛击后的战场应激创伤、日本屠城传统与高压武士道精神，以及指挥官更换——松井石根因生病被替换，朝香宫鸠彦亲王上任后发布“不留俘虏，月后祭坟”命令，导致军纪失控；其三，影片中中华门城墙战斗、挹江门撤退信息差惨案、战后审判枪决谷寿夫等主犯均为真实历史细节。
-关键锚点包括：**1937年8月13日**淞沪抗战、**松井石根**与**朝香宫鸠彦亲王**两位指挥官、**谷寿夫**（第六师团师团长）被枪决。对听众而言，这场讨论有助于区分电影艺术加工与历史事实，并理解南京大屠杀发生的多重历史动因，适合作为观影后的延伸学习材料。
+本次讨论由贝姐主持，围绕电影《南京照相馆》展开，参会者包括发言人2、发言人3、发言人4、发言人5。大家先分享了观影印象：发言人3在抖音看过切片、也去电影院看过，觉得挺好看；发言人4认为电影是灾难片，印象最深的是地下室多人吃喝睡觉的场景；发言人2觉得电影深刻好看；发言人5因题材不习惯未观看。贝姐随后介绍了南京大屠杀的历史背景，并澄清电影中主要人物为虚构，但照片拍摄真实——实际由两位美国传教士拍摄日军暴行，中国照片冲洗人员偷偷拷贝后于战后交给国民政府军事法庭作为审判日本战犯的证据。讨论覆盖了历史背景、电影虚构与真实细节、日军暴行原因分析、相关纪念馆参观经历等板块。核心判断包括：日军自九一八事变以来未遭成规模抵抗，在上海首次遭遇迎头痛击后产生应激创伤反应，加之指挥官更换（松井石根因生病被替换，接任者朝香宫鸠彦亲王发布“不留俘虏，月后祭坟”命令），导致军纪失控酿成南京大屠杀；电影中中华门城墙战斗、挹江门撤退惨案、战后对谷寿夫等主犯的枪决均为真实历史。
+关键锚点包括**1937年8月13日淞沪抗战**、**朝香宫鸠彦亲王**、**谷寿夫（第六师团师团长）**。对听众而言，本次讨论有助于理解南京大屠杀的历史成因与电影创作的真实性边界。
 # 核心观点与论证
-## 论点：电影《南京照相馆》的观影印象多元，题材沉重影响观看意愿
-- **发言人3**：在抖音看过切片觉得还行，后去电影院观看，认为挺好看；因话题太沉重，一般不愿主动去电影院看这类电影。
-- **发言人4**：认为电影是灾难片，最后老弱妇孺存活；印象最深的是地下室好几个人吃喝睡觉的场景。
-- **发言人2**：觉得电影挺深刻、挺好看，观看后感觉很悲痛。
-- **发言人5**：因题材不习惯未看过，连片段都没看，觉得特别悲痛。
-## 论点：南京大屠杀的历史背景——淞沪抗战失利与日军军纪失控
-- **1937年8月13日**，国民党军队在上海与日军激战（八一三淞沪抗战），后因各方面实力原因从上海撤退，日军紧随其后追击至南京。
-- 从**1931年九一八事变**到八一三淞沪抗战前，日军占领东北、华北均未遭遇成规模抵抗；淞沪抗战是日军入侵中国以来首次遭受的迎头痛击。
-- 日军因战场过于惨烈、伤亡惨重，加上从上海打到南京长达四个月战斗，缺乏军纪约束、已杀红眼，攻破南京后无人性约束，导致南京大屠杀发生。
-## 论点：电影虚构与真实——人物虚构，照片拍摄真实
-- 电影中主要人物为虚构，但照片拍摄是真实的，且并非以电影描述的方式进行。
-- 真实历史为**两名美国传教士**拍摄了日军暴行；同期中国负责给日本人冲洗照片的人员无意间发现这些暴行照片（当时在日本属禁文），偷偷拷贝藏起，战后递交国民政府军事法庭作为审判日本战犯的证据。
-## 论点：日军南京大屠杀的原因——轻敌、应激创伤、屠城传统与指挥官更换
-- 上海是中日第一场大规模战斗地点，日军自九一八事变以来未遭像样抵抗，在上海遭受迎头痛击后，从日军角度感到前所未有的侮辱及战场应激创伤反应。
-- 日本自古有攻破敌方城镇后屠城进行狂欢与麻痹的传统；加上从上到下高压武士道精神的欺凌霸凌背景，日军更想找宣泄口发泄。
-- 原日军指挥官**松井石根**因生病被临时替换，他是了解中国的皇道派军人，曾接连发布命令避免日军在上海至南京沿线烧杀抢掠，以免增强中国军民抵抗意志。
-- 替换者为裕仁亲王的叔叔**朝香宫鸠彦亲王**，他是脱亚入欧思想的狂热追随者，认为亚洲国家除日本外都低贱；上任后发布第一道命令「不留俘虏，月后祭坟」，导致日军格杀无论，蔓延至老百姓群体，最终酿成南京大屠杀。
-## 论点：电影中的真实历史细节——战斗、撤退惨案与战后审判
-- 电影开头**中华门城墙战斗**是真实历史细节，反映日军进攻南京所遭受的抵抗。
-- **挹江门**撤退时，宪兵未让军队和平民撤出，守军未收到撤退命令，两边信息差导致最终惨案。
-- 电影尾声审判为真实历史：打进南京的部队主犯如**谷寿夫**（第六师团师团长）及多名上新闻的基层日军军官被枪决。
-- **发言人5**指出：现在好多日本人还不承认南京大屠杀这件事。
-## 论点：相关纪念馆参观情况反映公众关注度
-- **发言人2**：去过沈阳伪满洲国博物馆，上午去下午根本排不上队，整个广场全是人，必须预约；唐山大地震纪念馆情况类似。
-- **发言人3**：去过上海淞沪会战相关纪念馆（四行仓库等），下大雨仍全是人，大人小孩都很多；认为上海宣传做得好，可能与党的诞生地有关；推测南京大屠杀纪念馆应有很大介绍，但很难抢票。
-- **发言人4**：多年前去过南京大屠杀纪念馆，当时还可以，里面有很多实验类展品；现在抢都抢不到。
+## 论点：电影《南京照相馆》的创作背景源于南京大屠杀历史
+- **历史背景**：1937年8月13日，国民党军队在上海与日军激战（八一三淞沪抗战），因实力原因从上海撤退后，日军一路追击至南京。
+- **日军心理状态**：自1931年九一八事变以来，日军占领东北、华北均未遭遇成规模抵抗；八一三淞沪抗战是日军首次遭遇迎头痛击，战场惨烈、伤亡惨重，长达四个月战斗后日军军纪失控、杀红眼，攻破南京后无法律军纪约束，导致南京大屠杀。
+- **电影虚实关系**：电影中主要人物为虚构，但照片拍摄是真实的，且拍摄方式与电影描述不同。
+## 论点：电影中照片的真实来源与电影情节存在差异
+- **真实拍摄者**：实际由两位美国传教士拍摄了日军暴行相关照片。
+- **照片流转过程**：中国负责给日本人冲洗照片的人员（类似照片冲洗工作）无意间发现日军拍摄的暴行照片，当时在日本属于禁文，他偷偷拷贝并藏起，抗战后递交给国民政府军事法庭，作为审判日本战犯的证据。
+- **电影改编**：电影将照片来源改编为片中人物拍摄留存，与真实历史不符。
+## 论点：日军南京大屠杀的深层原因包含心理、传统与指挥层更替
+- **日军心理与历史传统**：日军自九一八事变以来未遭像样的大规模战争，在上海遭受迎头痛击后产生应激创伤反应；结合日本历史上攻破敌方城镇后以屠城进行狂欢与麻痹的传统，以及高压武士道精神下的欺凌与霸凌背景，日军更想找宣泄口发泄。
+- **指挥官更替**：原指挥官松井石根因生病被临时替换，他曾发布命令避免日军在上海至南京沿线烧杀抢掠，以防增强中国军民抵抗意志；接任者为裕仁亲王的叔叔朝香宫鸠彦亲王，他是脱亚入欧思想的狂热追随者，认为亚洲国家除日本外都低贱。
+- **军纪失控**：朝香宫鸠彦上任后发布第一道命令“不留俘虏，月后祭坟”，日军第一时间格杀勿论，随后蔓延至对老百姓的暴行，最终导致南京大屠杀。
+## 论点：电影中的真实历史细节
+- **中华门城墙战斗**：电影开头中华门城墙的战斗是真实历史细节。
+- **挹江门撤退惨案**：军队和平民撤退时，宪兵未让撤出，守挹江门部队未收到撤退命令，两方信息差导致最终惨案。
+- **战犯审判**：电影尾声审判部分真实，打进南京的部队如谷寿夫（第六师团师团长）及上新闻的基层日军军官主犯被枪决。
+- **现实争议**：发言人5指出现在很多日本人不承认南京大屠杀。
 # 金句总结
-&gt; 从九一八事变以来，日本人夺取咱们国家很多地方的时候，可以说是兵不血刃的那么一个状态。
-&gt; 在战场上长达四个月的一个状态，已经杀红眼了，就是可以说是在战争底下那种人性的泯灭。
-&gt; 他上任之后发布的第一道命令就是不留俘虏，月后祭坟。
-&gt; 在这样的人作为统帅，结果自然可想而知。
-&gt; 从他们当时那样的一个心态来说，觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。
-&gt; 我兴许我活不到战争结束，那我就趁着我还活着的时候，我对自己进行一种放纵。
+&gt; 在战争底下就是那种人性的泯灭吧。
+- 背景：贝姐解释日军从上海追击至南京途中，因长达四个月战斗、伤亡惨重而军纪失控，最终导致南京大屠杀。
+&gt; 从他们当时那样的一个心态来说，就觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。
+- 背景：贝姐分析日军自九一八事变以来首次遭遇淞沪会战的迎头痛击后，心理上产生的创伤与报复心态。
+&gt; 因为从他自己的角度来说，就是说我兴许我活不到战争结束，那我就趁着我还活着的时候，我对自己进行一种放纵。
+- 背景：贝姐剖析日军攻破城镇后屠城狂欢的心理动机，结合日本历史传统与战场绝望感。
+&gt; 在他的眼里，整个亚洲国家除了日本以外，其他国家都是低贱的。
+- 背景：贝姐介绍接任日军统帅的朝香宫鸠彦亲王——裕仁亲王的叔叔，脱亚入欧思想的狂热追随者。
+&gt; 果然他上任之后发布的第一道命令就是不留俘虏，月后祭坟。
+- 背景：贝姐说明朝香宫鸠彦接替生病的松井石根后，第一道命令直接导致日军格杀勿论，蔓延至平民。
+&gt; 照片是真实发生的。
+- 背景：贝姐澄清电影中主要人物为虚构，但日军暴行照片的拍摄是真实历史，由两位美国传教士拍摄、中国照片冲洗人员偷偷拷贝后交给军事法庭。
 # Q&amp;A 环节
-**发言人4**：电影里那个日本军官和主角建立友谊的情节是虚构的吗？历史上有没有这样的日本军官？
-**贝姐**：电影里的主要人物是虚构的，但照片拍摄是真实的，只是不是以电影里描述的方式进行的。真实历史是两名美国传教士拍摄了日军暴行，同时期还有一位负责给日本人冲洗照片的中国后期人员，无意间发现这些在日本属于禁文的暴行照片，偷偷拷贝藏起来，抗战后递交给国民政府军事法庭，作为审判日本战犯的证据。
-**发言人5**：现在好多日本人还不承认南京大屠杀这个事情。
-**贝姐**：对。电影里真实的历史细节包括：开头中华门城墙的战斗是真实发生的；挹江门撤退时，宪兵没让平民和军队撤出去，守军没收到撤退命令，两边信息差导致惨案；电影尾声的审判也是真实的，打进南京的谷寿夫（第六师团师团长）等主犯被枪决。</t>
+**发言人4**：电影里虚构的部分，是不是有一个日本军官和主角建立友谊的情节？这个日本军官是真实的吗？
+**贝姐**：电影里的主要人物是虚构的，但照片的拍摄是真实的，只是方式与电影描述不同。真实历史是两位美国传教士拍摄了日军暴行；同时期，一位负责给日本人冲洗照片的中国后期人员无意间发现这些暴行照片，偷偷拷贝藏起，战后递交给国民政府军事法庭，作为审判日本战犯的证据。
+**发言人5**：现在好多日本人还不承认这个事情。
+**贝姐**：对。电影里真实的历史细节包括：开头中华门城墙的战斗是真实的；挹江门撤退时，宪兵没让平民撤出，守军未收到撤退命令，信息差导致惨案；电影尾声的审判部分也是真实的，谷寿夫（第六师团师团长）等主犯被枪决。</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>52.6</v>
+        <v>49.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4228/2616</t>
+          <t>4228/2395</t>
         </is>
       </c>
     </row>
@@ -16461,48 +16313,47 @@
       <c r="C49" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由发言人1主持引导、发言人2参与，共2人围绕日本国家概况展开自由漫谈。由头是发言人1提出日本在中国人印象中复杂——既有历史战争记忆，又是主要贸易伙伴和热门旅游目的地，遂邀请大家分享对日本的印象与了解。议题范围涵盖：日本文化的历史阶段与三次转型（大化改新、明治维新、和平宪法）、民族性格成因、天皇制度演变、君主立宪制对比，以及秋叶原、中古店、富士山等购物旅游话题。讨论以分享观点为主，未形成统一结论。关键锚点包括**三次历史转折**、**1945年**麦克阿瑟迫使天皇公开露面、**广场协议**后催生中古店产业。讨论按议题逐块推进，从文化历史切入，经天皇制度延伸至购物旅游，期间夹杂中英混杂的即兴交流。
+本次会议为自由讨论形式，由主持人（发言人1）发起，参与者为发言人2，共2人。讨论由主持人提出「谈一谈日本这个国家的一个概况，还有大家对日本的一个印象」开场，围绕**日本国家概况与历史阶段**、**日本天皇制度与君主立宪制**、**日本旅游与购物体验**三个议题展开。讨论梳理了日本文化的三次历史转折（大化改新、明治维新、和平宪法转型），并延伸至天皇地位变迁、中古店产业起源等话题。整体以分享观点为主，未形成统一结论。关键锚点包括：**三次历史转折**、**1945年**麦克阿瑟迫使天皇公开露面、**广场协议**后泡沫经济崩溃催生中古店产业。讨论由主持人按议题逐块推进，先概述历史脉络，再回应参与者提问，最后转向旅游购物体验，期间穿插中英混杂的即兴交流。
 # 发言要点
 ## 日本国家概况与历史阶段
-- **发言人1**：提出日本文化缺乏原创，属外来接收后的本土化转型，经历三次转折——大化改新时期、明治维新时期、二战后和平宪法转型时期。
-- **发言人1**：大化改新后日本大规模向中国、朝鲜半岛学习，在吴越文化基础上本土化转型，形成和服、制茶、漆器等传统印象。
-- **发言人1**：明治维新后日本积极向欧美列强看齐，借鉴英国和德国的法度；二战后美国制定和平宪法，社会结构大规模转型，向美国看齐。
-- **发言人1**：现代日本文化印象包括动漫、二次元、汽车工业和铁道工业，影响深远。
-- **发言人2**：读研时上过日本文化课，学习漆艺、茶艺等传统文化；读老舍《四世同堂》后，认为民族仇恨还是应有一定影响。
-- **发言人1**：回应称民族仇恨程度不如欧洲中亚地区严重，那些地区民族仇恨非常严谨。
-## 日本民族性格与天皇制度
-- **发言人2**：听过一种评论——日本是岛国，气候不稳定，如发展农业可能遭遇海啸，因此民族性格容易极端。
-- **发言人1**：古代天皇对各地封建君主而言类似吉祥物，如同东汉末年或战国时期的天子，被供奉为神灵以精神层面控制百姓。
-- **发言人1**：1945年二战后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，从精神上打破固有认知，推动社会转型。
+- **发言人1**：提出讨论日本概况，指出中日关系复杂——既有历史战争悲剧，日本又占中国外部投资很大比重、是主要贸易伙伴，且日本服务业和购物体验在各国中首屈一指。
+- **发言人2**：分享个人对日本文化的兴趣，读研时上过讲日本文化的课，读过老舍《四世同堂》后认为民族仇恨还是应该要有一点影响。
+- **发言人1**：日本文化没有原创，是外来接收后本土化改进的转型，追问发言人2所指具体是哪个历史阶段的日本文化。
+- **发言人2**：指日本传统文化与现代文化艺术，如漆艺、制茶茶艺，这些现在都是日本的文化标志。
+- **发言人1**：日本文化在吴越文化基础上本土化转型，经历三次转折——古代大化改新时期、近代明治维新时期、二战后和平宪法转型时期，各阶段衍生不同新兴文化。
+- **发言人1**：大化改新后日本大规模向中国和朝鲜半岛学习，形成和服、制茶、漆器等传统印象；明治维新后向欧美列强学习，借鉴英国和德国的法度；二战后美国制定和平宪法，社会结构大规模转型，积极向美国看齐。
+- **发言人1**：现代日本给我们的印象包括动漫、二次元、汽车工业和铁道工业，影响功不可没。
+- **发言人2**：听过一种评论，日本民族性格极端与其岛国气候不稳定有关——发展农业可能遭遇海啸等灾害，导致性格容易走极端。
+## 日本天皇制度与君主立宪制
+- **发言人1**：古代天皇对各地封建君主而言是吉祥物般的存在，类似东汉末年或战国时期的天子，不能退位，被当作神灵供奉，以此从精神层面控制老百姓。
+- **发言人1**：1945年二战结束后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，从精神上打破固有认知，推动社会转型。
 - **发言人2**：询问现在民众对天皇是否还有崇拜。
-- **发言人1**：现在天皇类似英国、西班牙君主立宪制，是象征性存在，不能参与政治，由国会和内阁选出首相执政；美国将日本改造成英美海洋法系国家结构。
-- **发言人1**：英国国王影响力大于天皇，因英国国王是英联邦国家（澳大利亚、新西兰、加拿大等）名义元首；日本只有本州岛范围，天皇无实权，靠政府养着。
-- **发言人1**：除日本、英国外，西班牙、泰国等也有皇室；体制上与日本较相近的是英国和西班牙。
-## 日本购物与旅游体验
-- **发言人1**：秋叶原以动漫、手办闻名，数码宝贝玩偶、铁甲小宝原装及黑暗战路暴龙兽合金版均为秋叶原最早发行。
-- **发言人1**：日本奢侈品便宜，中古店（Vintage shop）是二手奢侈品商店，源于广场协议后泡沫经济崩溃、上班族失业后寄卖奢侈品，催生该产业。
-- **发言人1**：上海有很多中古店，能买到LV、Burberry、古奇等上个世纪大牌；男性款式相对少，女性选择更多。
-- **发言人2**：去日本购物主要买化妆品、美妆、护肤品。
-- **发言人1**：去日本喜欢爬山（富士山）、看古城、逛博物馆，如镰仓、京都、名古屋等地；喜欢镰仓夏天凉爽的气候。
+- **发言人1**：已没有崇拜，类似英国和西班牙的君主立宪制——天皇及皇室成员不能参与政治，是象征性存在，政治由国会和内阁选出首相执政；美国把日本改造成英美海洋法系国家结构。
+- **发言人1**：天皇存在感不如英国国王——英国国王还是整个英联邦国家的名义元首（澳大利亚、新西兰、加拿大等），而日本只有本州岛范围，天皇没有任何实权，靠政府养着。
+- **发言人1**：除日本、英国外，西班牙也有皇室，泰国也有；教皇属于宗教领域而非国家体制；体制上与日本相近的是英国和西班牙。
+## 日本旅游与购物体验
+- **发言人1**：推荐日本城市长崎、东京、大阪，东京有美食、购物、博物馆；曾去过长崎，感觉该城市融合了东方文化和现代西方文化。
+- **发言人1**：秋叶原发行过数码宝贝玩偶、铁甲小宝原装、数码宝贝第二部黑暗战路暴龙兽合金版等手办。
+- **发言人1**：日本奢侈品便宜，还有Vintage shop中古店（二手奢侈品商店）；广场协议后日本泡沫经济一夜崩溃，上班族失业后寄卖原先购买的高档大衣、西装、皮具等，催生中古二手店产业。
+- **发言人1**：上海有很多中古店，能买到上个世纪LV、Burberry、古奇等大牌；男性款式相对少，女性购物选择多。
+- **发言人2**：去日本会买化妆品、美妆、护肤品；买手办可能不只去日本，法国、意大利、韩国也买得多。
+- **发言人1**：去日本最喜欢爬山（富士山）、看古城（镰仓、京都、名古屋）、逛博物馆；镰仓夏天气候比较舒服。
 # 共识形成
-- **一致意见**：日本文化缺乏原创性，属外来接收后的本土化转型，经历**大化改新、明治维新、和平宪法**三次历史转折；天皇现为象征性存在，无实权、不参与政治，由国会和内阁选出首相执政。
-- **倾向性认识**：发言人1与发言人2对日本民族性格成因形成倾向性看法——发言人2提出岛国气候不稳定（海啸等）可能导致民族性格极端，发言人1未反对并补充天皇制度演变作为佐证，双方在「地理环境影响民族性格」上方向一致。
-- **主要分歧点**：发言人2认为民族仇恨「还是应该要有一点影响」，发言人1则回应「咱们这还没那么严重」，并对比欧洲中亚民族仇恨更严重，双方对历史仇恨在当下应占多大分量存在程度差异。
-- **结论口径**：天皇制度方面，发言人1明确1945年二战后麦克阿瑟迫使天皇公开露面，打破「天皇是神灵」的认知；现天皇地位类似英国、西班牙君主立宪制，但影响力不及英国国王（因后者是英联邦名义元首），日本天皇「靠政府养着」。
+- **一致意见**：日本文化缺乏原创性，属于外来接收后的本土化转型，其传统标志（和服、制茶、漆器）源自唐朝吴越文化基础；现代日本印象集中于动漫、二次元、汽车工业和铁道工业。天皇制度方面，双方认可天皇现为象征性存在，不参与政治，政治由国会和内阁选出首相执政，日本被改造成英美海洋法系国家结构。
+- **倾向性认识**：发言人1系统梳理日本三次历史转折——**大化改新**（向中国和朝鲜半岛学习）、**明治维新**（向欧美列强学习，借鉴英国和德国法度）、**二战后和平宪法转型**（向美国看齐）。发言人2补充岛国地理与不稳定气候塑造日本民族性格易极端的观点，发言人1未明确反对。
+- **主要分歧点**：发言人2认为民族仇恨应对日本文化喜爱产生影响（受《四世同堂》启发），发言人1则强调日本文化影响深远、未正面回应此判断；关于民众对天皇的崇拜，发言人2质疑「现在没有崇拜了吗」，发言人1明确回答「没有了」，并对比英国国王因英联邦名义元首身份影响力更大，而天皇仅限本州岛范围。
 # 待探讨问题与后续
-- **未确认**：发言人1提问「日本文化具体指哪一个历史阶段的日本文化」，发言人2回应涵盖传统文化（漆艺、茶艺）与现代文化艺术，但未明确限定具体历史阶段，该问题未获完整答复。
-- **未确认**：发言人2询问「日本民众现在对天皇是否还有崇拜」，发言人1回答已无崇拜、天皇为象征性存在，但未展开民众实际态度层面的深入探讨。
-- **未确认**：发言人1提问「二次元用英语怎么表达」，现场未给出明确翻译，话题随即转向购物讨论。
-- **未定论**：发言人2提出「岛国气候不稳定导致日本民族性格极端」的观点，发言人1未直接回应或反驳，该观点未被进一步讨论或验证。
-- **未定论**：关于日本文化是否缺乏原创性、属外来接收后本土化转型的判断，发言人2未明确表态，仅以「日本文化对我们影响挺多」回应，双方未就此达成一致认识。</t>
+- **未确认**：日本文化具体指哪一个历史阶段的日本文化——发言人1在讨论中提出此问，发言人2回应涵盖传统文化（漆艺、茶艺）与现代文化艺术，但未就「日本文化」的界定范围达成明确结论。
+- **未确认**：日本民众对天皇的崇拜是否已完全消失——发言人2提出此问，发言人1回答称天皇已类似英国、西班牙君主立宪制下的象征性存在，但未提供民意调查或实证数据支撑，该问题仍属开放讨论。
+- **待核实**：二次元一词的英语表达——发言人1在讨论中询问「二次元用英语怎么表示」，发言人2未给出明确答案，该问题在会议中未获解决。</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>38</v>
+        <v>41.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4892/2231</t>
+          <t>4892/2477</t>
         </is>
       </c>
     </row>
@@ -16715,61 +16566,67 @@
       <c r="C50" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论为文学主题的延伸，由发言人1提议从《西游记》转入《三国演义》与《红楼梦》的分享。与会者共5人（发言人1至发言人5），以漫谈方式逐块推进：先聊三国印象、阵营偏好、正史与演义差异（赤壁之战、刘备称王、借荆州、白衣渡江、东吴大都督结局、魏延之死、三顾茅庐与诸葛亮北伐），再转入红楼梦的版本、判词、人物命运与悲剧走向。整体以分享观点为主，未形成统一结论。关键锚点包括：**前八十回**与后四十回作者差异、**第五回**太虚幻境判词、**香水之盟**（湘水划界）。讨论由发言人1主导提问，发言人2、3、4、5轮流回应，偶有发散（如曹雪芹小道），最后由发言人1提议暂停并进入下一话题。
+本次讨论为文学阅读分享的延伸场次，共5位发言人（发言人1至发言人5）参与，由发言人1提议从《西游记》延伸至《三国演义》与《红楼梦》两部经典。三国部分围绕印象最深的章节、阵营偏好、正史与演义差异展开，涉及赤壁之战、刘备称王连锁反应、吕蒙白衣渡江、东吴大都督结局、姜维北伐及三顾茅庐等议题；红楼梦部分聚焦版本问题（前八十回与高鹗续书）、第五回判词、人物命运解读及晴雯、袭人等角色映射。讨论以分享观点为主，未形成统一结论，整体呈漫谈发散式推进，由发言人1引导话题、发言人4建议轮流发言后逐步展开。关键锚点包括**诸葛亮去世**（发言人2阅读中断点）、**第五回判词**（红楼梦结局伏笔）及**高鹗续后四十回**（官方通行版本）。
 # 发言要点
 ## 三国演义印象与历史细节
-- **发言人2**：三国看到诸葛亮去世后就不想看了，认为后面内容基本没意思，后面讲啥都不知道；印象最深刻的章节是赤壁之战，认为前面比后面有意思。
-- **发言人2**：偏好蜀汉阵营，因刘备白手起家，受《三国演义》影响较大。
-- **发言人1**：补充正史后续——姜维北伐、孙权二宫之争（晚年昏庸害死两子致东吴朝廷大乱）、邓艾偷渡阴平、姜维反间计同归于尽、刘禅投降、西晋灭吴。
-- **发言人1**：认为刘备称汉中王不妥，封建礼治时期贸然称王引发连锁反应——吕蒙白衣渡江、刘备伐吴失败、夷陵惨败。
-- **发言人1**：澄清借荆州史实——孙权借南郡给刘备，刘备当老赖不还；孙权只要求交还部分地区，刘备不乐意，孙权派兵夺荆南三郡，刘备集结大军针锋相对；后因曹操攻汉中，刘备回师，双方签订香水化界（香水之盟）。
-- **发言人1**：单刀赴会实为鲁肃与关羽不带兵士、带随身随从在中立区谈判，被罗贯中美化为关云长只身赴险。
-- **发言人1**：刘备此举把孙刘联盟信任搞没；孙权打合肥不下，索性偷荆州袭关羽。
-- **发言人2**：白衣渡江伪装成商人打仗不道德，突破底线，口碑不好，开了坏头。
-- **发言人1**：吕蒙因白衣渡江被后世将「小偷鼠辈」与其名字画等号。
-- **发言人2**：对陆逊印象是火烧连营；东吴后期政治斗争严重，大都督内斗厉害，没几个善终。
-- **发言人1**：东吴大都督结局——周瑜正史被曹人射毒箭阵亡，鲁肃得瘟疫病故，吕蒙病故，陆逊在二宫之争时被孙权活活逼死（因陆逊问责孙权立太子后不应让两子相争）。
-- **发言人1**：刘禅自知能力不足完全放权诸葛亮；诸葛亮去世后姜维无法力挽狂澜，刘禅轻信黄皓谗言；姜维是魏国降将，若非诸葛亮提拔没有说服力，众人不服。
-- **发言人1**：魏延正史无谋反之心，只是不甘心大军撤退，烧毁悬崖栈道；若非姜维断后挡住司马懿军队，后果不堪设想——行为与谋反无实质区别，实为与杨仪个人矛盾上升至军队层面。
-- **发言人5**：简述三顾茅庐——刘备中原屡战屡败、深感缺乏谋士，经推荐得知诸葛亮有卧龙之才，携关羽张飞三次前往拜访（第一次诸葛亮外出、第二次恰逢风雪、第三次终见），诸葛亮被其打动提出隆中对战略，同意辅佐刘备。
-- **发言人1**：隆中对战略为横跨荆益、外结好孙权、西和诸戎、趁魏国变动北伐；白衣渡江后蜀汉失荆州全境，横跨荆益不成立，与结好孙权直接矛盾。
-- **发言人1**：诸葛亮北伐目标为关中平原和陇西（今陕西、甘肃南部），希望纵跨凉益以图中原；第一次北伐赢面大，因马谡兵败街亭而破产，后期北伐沦为绝望中的抗争、拖延魏国灭蜀时间。
+- **发言人2**：看到诸葛亮去世后便没再读下去，认为三国到诸葛亮去世已差不多讲完八九成，后面本来也没啥意思。
+- **发言人1**：补充正史后续脉络——姜维北伐、孙权晚年二宫之争害死两子致东吴朝廷大乱、邓艾偷渡阴平、姜维反间计自爆同归于尽、刘禅投降、西晋灭吴。
+- **发言人2**：印象最深刻的章节是赤壁之战，认为三国前面比后面有意思。
+- **发言人2**：偏好蜀汉阵营，因受《三国演义》影响，刘备算白手起家。
+- **发言人1**：认为刘备若未称汉中王，孙权可能不会与他彻底决裂；称王引发连锁反应——吕蒙白衣渡江、刘备伐吴失败致夷陵惨败。
+- **发言人1**：正史中孙权只要求刘备归还部分地区，刘备不乐意，孙权首次派兵强夺荆南三郡；后因曹操攻下汉中威胁西川，刘备回师救援，与孙权签订湘水划界（湘水之盟）。
+- **发言人1**：湘水划界对应关云长单刀赴会背景——实际是鲁肃与关羽各带随从在中立区谈判，被罗贯中美化为关羽只身赴险。
+- **发言人1**：刘备此举把孙刘联盟信任最后一点搞没；孙权打合肥不下，索性偷袭荆州、袭关羽。
+- **发言人2**：白衣渡江伪装成商人打仗不太道德、突破底线，开了个坏头。
+- **发言人1**：吕蒙白衣渡江开坏头——好歹当时还是盟友，偷盟友的家，后世把「小偷鼠辈」与吕蒙名字划等号。
+- **发言人2**：对陆逊印象只剩火烧连营和三国杀；东吴后期政治斗争严重、内斗狠，几个大都督没得好下场。
+- **发言人1**：东吴大都督结局——周瑜被曹人射毒箭阵亡，鲁肃得瘟疫病故，吕蒙病故，陆逊在二宫之争时被孙权活活逼死。
+- **发言人1**：陆逊因问责孙权「立了太子就不该让两子相争」而被逼死。
+- **发言人2**：蜀汉也内斗，魏延也是被砍的。
+- **发言人1**：刘禅自知能力不行，完全放权给诸葛亮；诸葛亮去世后姜维无力回天，且姜维是魏国降将，若非诸葛亮提拔没有说服力，众人不服他。
+- **发言人1**：魏延正史上没有谋反，只是不甘心大军撤退，烧了悬崖栈道；若非姜维断后挡住司马懿军队，后果不堪设想——无反心但行为与谋反无实质区别，实为与杨仪个人矛盾上升至军队层面。
+- **发言人5**：讲三顾茅庐——刘备中原屡战屡败、深感缺乏谋士，经人推荐得知隆中诸葛亮有卧龙之才，携关羽张飞三次拜访，前两次未遇，第三次得见，诸葛亮被其打动，提出隆中对战略（联合孙权），最终同意辅佐刘备。
+- **发言人1**：隆中对战略为横跨荆益、外结好孙权、西和诸戎、趁魏国有变北伐；白衣渡江后蜀汉失荆州全境，横跨荆益不成立，与结好孙权相矛盾。
+- **发言人1**：诸葛亮北伐目标在关中平原和陇西（今陕西、甘肃南部），希望纵跨凉益以图中原；第一次北伐赢面挺大，因马谡兵败街亭而破产，后期只能拖延魏国灭蜀时间，诸葛亮与姜维北伐更像绝望中的抗争。
 ## 红楼梦解读与版本
-- **发言人4**：红楼梦可当爱情小说看，讲贾宝玉、薛宝钗、林黛玉爱情故事，巧在没有解开的谜底。
-- **发言人3**：原著只写了前八十回，后面是别人写的。
-- **发言人2**：有反清复明版本解读，真正意义与当时社会有关。
-- **发言人4**：第一遍读高鹗续版本时觉得合理，当时不知道后四十回不是同一作者；反复读前八十回后发现林黛玉性格变化、贾母对林黛玉态度变化。
-- **发言人2**：前八十回有悲剧走向，开篇词有暗示，每个人都有判词。
-- **发言人3**：第五回贾宝玉梦游太虚幻境已以判词形式交代结局。
-- **发言人4**：判词没有点明，探春、史湘云结局都是猜的，最后谁和贾宝玉在一起不确定。
+- **发言人4**：红楼梦可从爱情小说角度读，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在它是一个没有解开的谜底。
+- **发言人3**：原著只写了前八十回，后面是别人续写。
+- **发言人2**：提到有版本说反清复明，但真正的意义估计与当时朝代、当时社会有关。
+- **发言人4**：第一遍读高鹗续本时不知道后四十回非同一作者，觉得挺合理；后来反复读前八十回再接触续本，发现林黛玉性格变了很多，贾府对林黛玉的态度也变了。
+- **发言人3**：第五回贾宝玉梦游太虚幻境已把结局交代了，以判词形式。
+- **发言人4**：判词没有点得那么明确，探春、史湘云的结局都是猜的，最后谁和贾宝玉在一起也说不准。
 - **发言人5**：问悲剧原因——贾宝玉与林黛玉真心相爱却被迫娶薛宝钗。
-- **发言人4**：林黛玉之死是后四十回内容，非原作所写，但原作意图肯定是悲剧。
-- **发言人4**：晴雯是林黛玉的替身，性格像黛玉；袭人性格像薛宝钗；晴雯之死是曹雪芹亲写，映照后续。
-- **发言人2**：有解读称林黛玉代表明朝、薛宝钗代表清朝。
-- **发言人4**：有人解读秦可卿是前朝公主；秦可卿是十二金钗正钗之一，可惜早逝。
-- **发言人4**：第五回贾宝玉在秦可卿床上睡觉做梦游太虚幻境，看到十二正钗（小姐）与副钗（丫鬟）判词，对应各人命运。
+- **发言人4**：林黛玉之死是后四十回内容、非原作所写，但原作意图肯定也是悲剧。
+- **发言人4**：晴雯是林黛玉的替身，性格像林黛玉；袭人性格像薛宝钗；晴雯之死是曹雪芹写出来的，映照后面林黛玉的命运。
+- **发言人2**：提到解读说林黛玉代表明朝、薛宝钗代表清朝。
+- **发言人4**：还有人解读秦可卿是前朝公主，但她也是金陵十二钗正钗之一。
+- **发言人4**：第五回贾宝玉在秦可卿床上睡觉做梦到太虚幻境，看到判词——十二金钗分正钗（小姐）与副钗（丫鬟），判词对应每个人命运。
 - **发言人2**：问为何选高鹗后四十回作为官方结尾。
-- **发言人4**：高鹗续写总体合理，官方说法是在残稿上梳理完善，未违背作者原意，但诗词能力不及曹雪芹。
-- **发言人3**：北京植物园附近有曹雪芹小道，旁边村子有相关遗迹。
-- **发言人2**：提到曹雪芹小道在植物园附近，樱桃沟一带。
+- **发言人4**：因其总体比较合理，官方说法是在残稿上梳理完善、未违背作者原意，但写作细节和诗词能力不及曹雪芹。
+- **发言人2**：提到曹雪芹小道，去过一个地方有曹雪芹什么道。
+- **发言人3**：曹雪芹小道就在北苑所旁边村子，之前爬山看到过。
+- **发言人4**：北京植物园里有曹雪芹故居。
 # 共识形成
-- **一致意见**：与会者普遍认为《三国演义》前半部分比后半部分精彩，发言人2明确表示看到诸葛亮去世后便不再阅读，认为后续内容无趣；对**赤壁之战**印象深刻。关于《红楼梦》，多人认同原著仅前八十回为曹雪芹所写，后四十回为他人续作，且原作意图为悲剧。
-- **倾向性认识**：发言人1与发言人2对刘备评价存在分歧——发言人2因刘备白手起家而偏好蜀汉阵营，发言人1则认为刘备贸然称汉中王不妥，引发白衣渡江、夷陵惨败等连锁反应，并指出借荆州一事中刘备当老赖不还，将孙刘联盟信任消耗殆尽。对白衣渡江，发言人2认为伪装商人打仗突破底线、不道德，发言人1补充吕蒙因此被后世视为小偷鼠辈。
-- **分歧点**：关于《红楼梦》结局，发言人3认为第五回判词已交代结局，发言人4则认为判词不明确，探春、史湘云结局及贾宝玉最终与谁在一起均属猜测；发言人2提出林黛玉代表明朝、薛宝钗代表清朝的反清复明解读，发言人4未明确认同，仅补充秦可卿被解读为前朝公主的说法。
+- **一致意见**：与会者普遍认为《三国演义》前段（至诸葛亮去世）比后段更有意思，发言人2明确表示看到诸葛亮去世后便未再读下去，认为后续内容缺乏吸引力；对赤壁之战印象深刻，并倾向蜀汉阵营，因刘备白手起家。
+- **倾向性认识**：发言人1与发言人2对吕蒙白衣渡江评价一致，认为伪装商人偷袭盟友突破底线、开了坏头，后世将吕蒙与「小偷鼠辈」等同；对东吴大都督结局形成共识——周瑜被曹人射毒箭阵亡、鲁肃病故、吕蒙病故、陆逊被孙权在二宫之争中逼死。
+- **主要分歧点**：发言人1认为刘备称汉中王是孙刘决裂的导火索，引发白衣渡江与夷陵惨败的连锁反应；发言人2则强调蜀汉同样内斗（魏延被砍），双方对蜀汉与东吴内部矛盾孰轻孰重未达成一致。
+- **红楼梦部分**：发言人4与发言人3一致认为原著仅前八十回、后四十回为高鹗续写，且第五回判词已交代结局方向；但发言人2对高鹗续本合理性存疑，发言人4回应称其总体合理、官方说法未违背作者原意，此点未再深入。
 # 待探讨问题与后续
-- **未确认**：发言人2对《红楼梦》后四十回为何选高鹗续本作为官方结尾存疑，发言人4回应称其总体合理、官方说法为在残稿上梳理完善且未违背作者原意，但诗词能力不及曹雪芹，此判断仍属个人解读，未形成定论。
-- **未定论**：关于《红楼梦》人物结局，发言人4指出判词未点明探春、史湘云结局，最后谁与贾宝玉在一起均属猜测；发言人2提及林黛玉代表明朝、薛宝钗代表清朝的反清复明解读，发言人4补充秦可卿被解读为前朝公主，此类索隐式解读未获与会者一致认可。
-- **待核实**：发言人2提到北京植物园附近有曹雪芹小道，发言人3称曾在北苑所旁边爬山时见过，但未确认其具体位置与历史依据。
-- **未定论**：发言人1认为刘备称汉中王引发孙权决裂、白衣渡江、夷陵惨败等连锁反应，此系个人史观判断，与会者未就此展开进一步讨论或达成一致。
-- **后续约定**：会议末尾，发言人1提议暂停并进入下一个话题，发言人3表示可以继续，但未明确下一话题的具体内容与时间安排。</t>
+- **未定论**：发言人2对《红楼梦》后四十回续写内容表示「没看明白他到底是想说啥」，对高鹗续本作为官方结尾的合理性存疑，但未展开进一步讨论。
+- **未确认**：发言人2提到「林黛玉代表明朝、薛宝钗代表清朝」的解读，发言人4对此未置可否，该说法未获在场成员认可或反驳，属于被搁置的解读话题。
+- **待核实**：发言人2提及「曹雪芹小道」位于植物园附近，发言人3称在北苑所旁边爬山时见过，发言人4称北京植物园内有曹雪芹故居，三处地点是否同一位置未达成一致，未进一步核实。
+- **未定论**：发言人4指出探春、史湘云等金陵十二钗的结局仅以判词形式暗示，具体结局「都是猜的」，未有人给出明确结论。
+- **未确认**：发言人4提到晴雯是林黛玉的「替身」、袭人性格似薛宝钗，此说法仅作为个人解读提出，未获其他成员明确认同或讨论。
+- **未定论**：发言人1分析刘备若未称汉中王可能避免孙权决裂，此假设性判断属个人观点，未获其他成员回应或验证。
+- **后续约定**：发言人1在三国讨论结束后提议「下一个话题」，发言人3回应「咱们可以继续」，但未明确下一话题内容或具体安排。</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>65.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6453/3031</t>
+          <t>6453/3242</t>
         </is>
       </c>
     </row>
@@ -16886,50 +16743,47 @@
       <c r="C51" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由**发言人1**发起，**发言人2**与**发言人3**参与，共3人，围绕三国战役的兵法战法与人物评价展开漫谈式交流。讨论由赤壁之战切入，因前序已聊完《红楼梦》《三国》《水浒》《西游记》《金瓶梅》，故延伸至三国故事线的战法分析。议题依次涉及：**赤壁之战的影响**、**合肥之战与孙权评价**、**火烧连营与陆逊评价**、**三国人物军事能力评价**。整体以分享观点为主，未形成统一结论；发言人对赤壁之战曹军败因、孙权军事才能等有倾向性看法，但未达成一致。关键锚点包括**公元215年合肥之战**、**张辽率800死士**、**火烧连营七百里**。讨论按议题逐块推进，由发言人1主导讲述史实并提问，发言人2、发言人3穿插补充看法与质疑，整体呈发散漫谈状态。
+本次讨论由发言人1发起，延续此前《红楼梦》《三国》《水浒》《西游记》《金瓶梅》的系列话题，聚焦三国战役的兵法和战法影响。参与成员共3人，以发言人1为主讲，发言人2、发言人3穿插回应。议题依次为：赤壁之战的影响、合肥之战与孙权评价、火烧连营与陆逊评价、孙权早期败仗与人物评价、诸葛亮北伐街亭失守假设。讨论以分享观点为主，未形成统一结论，整体倾向认为赤壁之战曹操败于骑兵不擅水战而非实力不济，对蜀汉和曹魏印象好于东吴。关键锚点包括**公元215年合肥之战**、**张辽800死士**、**火烧连营七百里**。讨论由发言人1按战役逐块推进，发言人2、发言人3在个别节点插话补充或质疑，整体呈漫谈发散状态。
 # 发言要点
 ## 赤壁之战的影响
-- **发言人1**：赤壁之战曹军败因在于不擅水战——曹操军队以虎豹骑为主、擅长陆战，刚收服荆州没有像样水军，而江东以水军为主；长江过不去，相当于渡海攻坚战规格，并非曹军实力不行。
-- **发言人1**：东吴北伐路线受制于合肥——从建业（今南京）过长江，经巢湖上岸，打下合肥后才能靠近淮河继续北进；孙权一生都在朝打合肥努力，但从未打下。
-- **发言人2**：对赤壁之战影响表示「不好说」，未展开具体主张。
+- **发言人1**：赤壁之战曹操失败的主因是**虎豹骑擅长陆战**，刚收服荆州没有像样水军，面对长江如同渡海攻坚战，过不去是兵种短板而非实力不济。
+- **发言人1**：东吴北伐路线必须从建业（今南京）过长江，经巢湖上岸攻下合肥，才能靠近淮河继续北上，合肥如钉子钉在路线上。
+- **发言人1**：孙权一生致力于攻打合肥但从未成功，公元215年合肥之战动员所有武将进攻，曹军主力在汉中，合肥仅张辽、李典、乐进三将镇守。
+- **发言人2**：对孙权评价「小时候觉得厉害，长大以后感觉反转比较厉害」，认同其打仗能力受质疑。
 ## 合肥之战与孙权评价
-- **发言人1**：公元215年合肥之战，孙权动员所有武将进攻合肥；曹军主力在汉中，合肥仅张辽、李典、乐进三员大将镇守，且三人间矛盾深重（张辽原属吕布，与乐进、李典不和）。
-- **发言人1**：张辽率800死士骑马向吴军冲锋，吴军未及反应大败而归，孙权差点被俘——张辽通过被俘吴军描述（马骑得好、箭射得准、上身长下身短、留小胡子）认出孙权，后悔没抓住，由此有「张八百大破孙十万」段子。
-- **发言人1**：张辽威震合肥，城内小孩不敢啼哭；后人称孙权「合肥战神孙十万」，正面打不过敌人、偷盟友家专业，成为后人吐槽点。
-- **发言人1**：孙权陵墓确切位置已找不着，南京紫金山立碑标注大概位置，碑前堆满张辽的影视海报和游戏卡片。
-- **发言人2**：小时候看「生子当如孙仲谋」觉得孙权厉害，长大后观感反转，认为他不只是「孙十万」的问题。
-- **发言人3**：孙权在孙十万之前也打过一场很坑的仗——几万人打人家，被几千人追着打；具体对手记不清，不是刘表、不是张辽，时间在赤壁之战前（发言人1推测可能是周瑜与曹仁作战时期，未确认）。
+- **发言人1**：张辽率**800死士**骑马向吴军冲锋，孙权优势兵力下大败，留下「张八百大破孙十万」段子；张辽、李典、乐进三人矛盾深重，张辽原属吕布部下。
+- **发言人1**：孙权在合肥城外扎营时，张辽突袭，吴军未及反应；张辽不认识孙权，战后询问俘虏「马骑得好、箭射得准、上半身长下半身短、留小胡子的人是谁」，得知是孙权后后悔差点抓住他。
+- **发言人1**：合肥城内张辽「跺两脚连小孩都不敢啼哭」，后人吐槽孙权「正面打不过、偷盟友家专业」，南京紫金山孙权墓确切位置已找不着，仅立碑纪念，碑前堆满张辽的影视海报和游戏卡片。
 ## 火烧连营与陆逊评价
-- **发言人1**：刘备因体恤下属，不忍酷暑折磨，让士兵在密林扎营抵御酷暑；陆逊抓住秋季干燥、树叶飘落时机，一口气放火，连营七百里被烧光，刘备只身逃回白帝城。
-- **发言人2**：提及陆逊与孙家有仇的说法（陆家和孙家没听过）。
-- **发言人1**：陆逊是江东四杰之一；孙策因被称为小霸王、过于冒失而被刺杀；曹操说「生子当如孙仲谋」是因为孙权开疆拓土不行但能守家业，对比曹操诸子最争气。
-## 三国人物军事能力评价
-- **发言人3**：从南往北打的成功案例少，除朱元璋外不多见；刘备至少汉中之战打得挺好，孙权打仗确实打得颓。
-- **发言人1**：夷陵之战刘备被仇恨冲昏头脑、冒失冒进；汉中之战有法正和黄权辅佐，靠地势地利把曹操耗出汉中，勉强打赢。
-- **发言人1**：关羽很厉害——水淹七军之外，阵中斩将是历史第一人，直接改变战场局势；自己阵营队友不争气，不是关羽能力不行。
-- **发言人3**：对关羽只知水淹七军；斩颜良诛文丑属个人战力而非部队打仗；黄忠阵斩夏侯渊与关羽不同（关羽是摆好阵后斩将，黄忠可能是从山上冲下来）。
-- **发言人3**：张飞无经典战役，只知道长坂坡；发言人1补充演义中张飞与马超在成都城下大战五百回合。
-- **发言人1**：曹操五子良将包括张辽（从吕布降来）、曹仁、夏侯渊、张郃、徐晃、于禁；于禁被关羽生擒；曹操血厚人多，耗得起。
-- **发言人1**：若诸葛亮第一次北伐用魏延守街亭，大概率能反杀张郃，不会像马谡那样轻易丢掉街亭，北伐第一次可能成功；但魏延想法大胆，不符合蜀汉当时实际支撑。
-- **发言人3**：认同魏延守街亭假设，但指出蜀汉地盘太小。
+- **发言人1**：刘备体恤下属，不忍酷暑折磨，令士兵在密林扎营抵御炎热，被陆逊抓住秋季干燥、树叶飘落的时机放火，**连营七百里**被烧毁，刘备只身逃回白帝城。
+- **发言人2**：提及「陆逊和孙家有仇」，发言人1回应陆逊是**江东四杰**之一，孙策因冒失被刺杀，曹操说「生子当如孙仲谋」是因孙权能守住家业，比曹操诸子争气。
+## 孙权早期败仗与人物评价
+- **发言人3**：孙权在孙十万之前也打过败仗，几万人被几千人追着打，对手名字记不清（疑似刘繇），发言人1追问是孙坚时期还是孙策刚死时期，双方未能确认具体人物。
+- **发言人3**：对蜀汉和曹魏印象更好，「曹操明着来，不像孙十万喜欢偷家」；刘备至少汉中之战打得挺好。
+- **发言人1**：刘备夷陵之战被仇恨冲昏头脑冒进，汉中之战有法正、黄权辅佐，靠地势地利把曹操耗出汉中。
+- **发言人1**：关羽很厉害，水淹七军、斩颜良诛文丑，**阵中斩将是历史第一人**，直接改变战场局势；队友不争气非能力不行。
+- **发言人3**：张飞没有经典战役，只知道长坂坡；发言人1补充演义中张飞与马超在成都城下大战五百回合。
+- **发言人3**：提及五子良将（张辽、曹仁、夏侯渊、张郃、徐晃、于禁），于禁被关羽生擒；发言人1认为曹操「血厚人多耗得起」。
+## 诸葛亮北伐街亭失守假设
+- **发言人1**：若诸葛亮第一次北伐用魏延守街亭，大概率能反杀张郃，不会像马谡那样轻易丢掉街亭，北伐可能成功；但魏延想法大胆，不符合蜀汉实际支撑。
+- **发言人3**：认同蜀汉「地盘太小」是根本制约。
 # 共识形成
-- **一致意见**：赤壁之战曹军败于不擅水战，而非实力不济——曹操军队以虎豹骑为主、擅长陆战，刚收服荆州后没有像样的水军，江东则以水军为主，双方水陆战差异是核心原因；东吴北伐必须过合肥，孙权一生致力于攻打合肥但从未成功。
-- **倾向性认识**：对孙权军事才能评价偏低，发言人1、发言人2、发言人3均认可其合肥之战的败绩，后人称其为“合肥战神孙十万”；对关羽评价较高，发言人1认为关羽“阵中斩将”是历史第一人，水淹七军为经典战绩，其失败在于“阵营内的队友不争气，不是说关羽能力不行”。
-- **主要分歧点**：发言人3提出孙权在合肥之战前还打过一场败仗，以数万人被几千人击败，但**具体对手与时间未确认**——发言人1先后猜测为刘表、张辽、曹仁、刘琦时期，发言人3均未确认，仅表示“不是刘表”“不是张辽”“曹仁那个还要早，没有赤壁之战”，最终未定论。
+- **一致意见**：与会者对赤壁之战与合肥之战的军事逻辑形成共识——曹操赤壁之败在于以虎豹骑为主的骑兵不擅水战，而非实力不济；东吴北伐受制于合肥这一“钉子”，孙权一生未能攻克，公元215年合肥之战中张辽率**800死士**大败孙权，留下“**张八百大破孙十万**”的典故。对火烧连营的定性也一致：刘备因体恤下属令士兵在密林扎营，被陆逊趁秋季干燥放火，**连营七百里**被烧毁，刘备只身逃回白帝城。
+- **倾向性认识**：整体对蜀汉和曹魏印象更好，认为曹操“明着来”，孙权“喜欢偷家”；发言人1认为关羽武艺高强，曾水淹七军、阵中斩将，但队友不争气；刘备汉中之战表现尚可，有法正、黄权辅佐。
+- **主要分歧点**：发言人3质疑关羽“打过啥”，仅认可水淹七军，认为阵中斩将属个人战力而非部队作战；发言人1则强调关羽阵中斩将是“历史第一个”直接改变战场局势。对孙权早期败仗，发言人3提及孙权曾被刘繇（或类似名字）以几千人击败数万人，但具体人物双方均未确认。
 # 待探讨问题与后续
-- **未确认**：发言人3提到的孙权早期败仗的具体对手是谁（原文仅提及「刘刘油」「刘有」等不确定表述，未能确认具体人名）。
-- **待核实**：发言人3提到的孙权早期败仗的具体时间（原文仅提及「孙策刚死的时候」，未能确认确切年份）。
-- **未定论**：关于孙权早期败仗的讨论中，发言人3与发言人1未能就对手身份达成一致，发言人1先后猜测「刘表」「张辽」「曹仁」「刘琦」等，均未获发言人3确认。
-- **未定论**：对关羽「阵中斩将」是否为历史第一人的说法，发言人3提出疑问，发言人1坚持该说法，双方未进一步核实。
-- **未定论**：关于诸葛亮第一次北伐若用魏延守街亭能否成功的假设性讨论，发言人1认为「大概率能反杀张郃」，发言人3仅回应「这地盘太小了」，未形成一致看法。</t>
+- **未确认**：发言人3提及孙权在孙策刚死时期曾被某位将领以几千人击败数万人，但该将领姓名（刘繇或类似名字）未能确认，发言人1先后猜测刘表、张辽、曹仁、刘琦等均被排除，最终未定论。
+- **未确认**：张飞是否有经典战役未达成一致，发言人3仅知长坂坡，发言人1补充演义中张飞与马超大战五百回合，但正史战绩未确认。
+- **未定论**：诸葛亮第一次北伐若由魏延守街亭能否反杀张郃，发言人1认为大概率能成功，但魏延想法大胆、不符合蜀汉实际支撑，且蜀汉地盘太小，该假设未深入展开。
+- **未定论**：孙权早期败仗的具体时间线与对手，发言人3与发言人1就战役发生在赤壁之前还是之后、对手是否为刘繇等反复核对，未能确认。</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>45.9</v>
+        <v>45.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4899/2500</t>
+          <t>4899/2322</t>
         </is>
       </c>
     </row>
@@ -16992,55 +16846,54 @@
       <c r="C52" t="inlineStr">
         <is>
           <t># 讲座概况
-本次研讨会由主讲人（发言人1）讲解1979年至1989年苏联入侵阿富汗的苏阿战争，以研讨会形式展开，面向对冷战史与地缘政治感兴趣的听众。讲座围绕阿富汗的地理战略位置、历史背景、苏联出兵原因、战争过程、各方援助及撤军原因等板块展开，并设问答环节解答听众疑问。
-讲座的核心判断有三：其一，阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为“亚洲的中间走廊地带”，是兵家必争之地；其二，阿富汗国土**90%为高原山地**，易守难攻，素有“帝国坟场”之称；其三，苏联因阿明过度导向美国而于**1979年12月24日平安夜**出兵，一夜控制喀布尔，扶植卡尔迈勒上台，最终因阿富汗人民战争消耗与士气低落，于**1989年**撤军。关键锚点包括基辛格评价阿明“用苏联的火柴点美国的香烟”、中国援助五六式冲锋枪与五六式半自动步枪、美国提供毒刺防空导弹压制苏联雌鹿武装直升机。
-对听众而言，本讲有助于理解冷战时期大国博弈逻辑、阿富汗“帝国坟场”的地理与制度根源，以及游击战对重装部队的制衡作用。
+本次研讨会由主讲人（姓名未提及）围绕1979年至1989年苏联入侵阿富汗的苏阿战争展开讲解，面向对冷战史与地缘政治感兴趣的听众。讲座覆盖阿富汗的地理战略位置与历史背景、苏联出兵原因、战争过程及各方援助、阿富汗为何难打及“帝国坟场”称号由来等板块。核心判断有三：其一，阿富汗地处亚洲中部，东接中国、北邻塔吉克斯坦、南接巴基斯坦与伊朗，被称为“亚洲的中间走廊地带”，是兵家必争之地；其二，其国土纵深**90%为高原山地**，除喀布尔、坎大哈等主要城市外，广大乡村由部落长老制控制，政府无力管辖，构成天然游击战环境；其三，苏联军事实力庞大但重装武器在高原山地难以发挥，基层官兵厌战、士气低落，最终在各方援助下的十年游击战消耗中于**1989年撤军**。关键锚点包括**1979年12月24日平安夜**苏联以“阿富汗请求救援”为由兵变突入、处决国王阿明并扶植卡尔迈勒上台，以及美国援助的**毒刺防空导弹**有效压制苏军“雌鹿”武装直升机。讲座对听众理解冷战格局下大国干预的代价及阿富汗长期动荡的地缘根源具有参考意义。
 # 核心观点与论证
-## 论点：阿富汗的地理位置与地形决定了其战略价值与“帝国坟场”属性
-- **地理位置**：阿富汗位于亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为“亚洲的中间走廊地带”，是兵家必争之地。
-- **地形特征**：国土**90%为高原山地地带**，易守难攻，是天然的游击战地区；历史上大英帝国入侵后曾被反推回巴基斯坦地区，阿富汗由此获得“帝国坟场”称号。
-- **治理结构**：除喀布尔、坎大哈等主要城市外，**90%地区实行乡村部落长老制**，政府无控制力，各村落部落各自为政，导致列强与城市政府均无法有效控制广大高原山地。
-## 论点：苏联出兵阿富汗是地缘战略与冷战逻辑共同作用的结果
-- **战前态势**：20世纪50年代阿富汗同时与苏联及西方国家保持友好，实行君主立宪制；国内精英奉行亲英与亲苏两头政策，文化上师从英国（议会制度、君主立宪、大学现代科学），国家建设与工业向苏联看齐。
-- **阿明的“墙头草”行为**：基辛格评价国王阿明“用苏联的火柴点美国的香烟”，两边同时要援助；阿明对苏联干涉内政不满并过度导向美国，引发苏联领导层不满。
-- **苏联的战略判断**：若阿富汗脱离苏联掌控倒向美国，将对苏联中亚地区形成被动局面；苏联高层政治局决定在阿富汗彻底导向美国之前，以兵变和武力介入。
-- **出兵过程**：**1979年12月24日平安夜**，苏联以“阿富汗请求救援”为由，从东部、中部、西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗变为傀儡。
-- **冷战背景**：当时处于**苏攻美守时期**，苏联咄咄逼人进行意识形态扩张与军事霸权恐吓，共同促成出兵；发言人3补充，按勃列日涅夫逻辑，不允许苏联阵营成员外出，如同此前出兵捷克，阿富汗是必须下场的战略要地。
-## 论点：国际社会合力援助阿富汗抵抗力量，苏联陷入十年游击战消耗
-- **国际反应**：苏联入侵招致众多阿拉伯国家、中国及西方盟国共同不满，各方合力援助阿富汗；阿富汗和穆斯林国家出动兵源，中国和西方盟国提供武器与情报资源，形成秘而不宣的默契。
-- **中国援助**：中国帮助阿富汗圣战抵抗者，教授抗战时期的地道战、地雷战等战法；提供与AK-47同型号的**五六式冲锋枪和五六式半自动步枪**，同时稀释国内已饱和的军工业；只提供军火和专家教兵法，未派人参战。
-- **美国援助**：美国援助先进单兵武器，如**毒刺防空导弹**（类似火箭筒的防空导弹），有效压制苏联当时最先进的**雌鹿武装直升机**；坦克和步兵战车在高原山地无法形成有效战斗力，需以步兵加武装直升机作战。
-- **圣战者抵抗**：阿富汗圣战者具有狂热的伊斯兰圣战思想，从上到下宗教式洗脑，抱着同归于尽的思想作战，类似二战日本军国主义荼毒下的日本军民。
-- **苏军困境**：苏联基层官兵普遍厌战，不明白为何来此战斗，士气一落千丈；苏联军事实力看似庞大，但武器在高原山地发挥不了作用，扛不住阿富汗人民战争的消耗。
-## 论点：苏联最终于1989年撤军，阿富汗战争成为其战略失误
-- **撤军结果**：苏联扛不住阿富汗人民战争的汪洋大海，最终于**1989年**从阿富汗撤出。
-- **战略定性**：发言人3指出，阿富汗是特殊战略要地，加上苏联的错判，导致其**大大的战略性失误**。
+## 论点：阿富汗的战略地位与“帝国坟场”称号
+- **地理枢纽**：阿富汗位于亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为“亚洲的中间走廊地带”，是名副其实的兵家必争之地。
+- **易守难攻**：国土纵深**90%为高原山地地带**，是天然游击战地区；历史上大英帝国入侵后曾被反推回巴基斯坦地区，阿富汗由此多次获得“帝国坟场”称号。
+## 论点：苏联出兵阿富汗的决策逻辑
+- **战前平衡**：20世纪50年代阿富汗同时与苏联及西方国家保持友好，实行君主立宪制；国内精英奉行亲英与亲苏两头政策，文化上师从英国（议会制度、君主立宪、大学现代科学），国家建设和工业方面向苏联看齐。
+- **阿明转向**：基辛格评价国王阿明“用苏联的火柴点美国的香烟”；阿明对苏联日益干涉内政不满、过度导向美国，苏联高层担心阿富汗脱离掌控将使其中亚地区陷入被动，决定在阿富汗彻底导向美国前以兵变和武力介入。
+- **军事介入**：**1979年12月24日平安夜**，苏联以“阿富汗请求救援”为由，从东部、中部、西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗变为傀儡。
+## 论点：国际社会共同援助阿富汗抵抗苏联
+- **多方合力**：众多阿拉伯国家、中国和西方盟国共同不满苏联举动，达成默契——阿富汗和穆斯林国家出动兵源，中国和西方盟国提供武器与情报资源，支持阿富汗抵抗组织进行长达十年的游击战争。
+- **中国援助**：中国教阿富汗圣战者抗战时期兵法（地道战、地雷战），援助与AK47同型号的五六式冲锋枪和五六式半自动步枪，通过援助稀释已饱和的军工业；只提供军火、未派人，但派专家教兵法，与西方盟国达成秘而不宣的默契。
+- **美国援助**：美国援助先进单兵武器，如`毒刺防空导弹`（类似火箭筒的防空导弹），有效压制苏联当时最先进的武装直升机“雌鹿”；坦克和步兵战车在高原山地无法形成有效战斗力，需以步兵加武装直升机作战。
+## 论点：阿富汗难以被外部力量控制的原因
+- **部落割据**：除喀布尔和坎大哈等主要城市外，**90%地区为乡村部落长老制**，政府无控制力，各村落部落各自为政，任何列强及城市政府都无法对广大高原山地形成有力控制。
+- **苏军困境**：苏联军事实力看似庞大但武器在高原山地无法发挥，基层官兵普遍厌战、不明白为何而战，士气一落千丈，最终于**1989年**扛不住压力撤军。
 # 金句总结
 &gt; 阿富汗多次获得其帝国坟场的称号。
-&gt; 基辛格评价阿富汗当时的总统阿明，说是用的苏联的火柴在点的美国的香烟。
+&gt; 背景：主讲人讲到历史上大英帝国入侵阿富汗被反推回巴基斯坦地区时，以此引出阿富汗易守难攻的地理特征。
+&gt; 基辛格评价阿富汗国王阿明是“用苏联的火柴点美国的香烟”。
+&gt; 背景：主讲人描述20世纪50年代阿富汗同时向苏联和西方国家两边要好处的墙头草外交姿态时引用。
 &gt; 谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-&gt; 这个国家相对来说是个贫油国，但它周边的国家都是富油国。
-&gt; 它除了以喀布尔和坎大哈那几个主要城市为首的城市地区以外，剩下大部分百分之九十的地区都是乡村部落长老制的那种制度。
+&gt; 背景：回答听众“阿富汗到底有啥好”的提问，解释其兵家必争之地的战略位置。
+&gt; 它这个国家相对来说是个贫油国，但它周边的国家都是富油国。
+&gt; 背景：回应听众关于阿富汗是否有石油的疑问，说明其自身贫油但周边（伊朗、土库曼斯坦、塔吉克斯坦）富油。
+&gt; 阿富汗百分之九十都是处于高原山地地带，就是一个天然的游击战地区。
+&gt; 背景：解释阿富汗为何难打、为何被称为帝国坟场时，点明其地理条件对游击战的天然适配。
 &gt; 苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。
+&gt; 背景：主讲人总结苏联重装部队在阿富汗高原山地无法形成有效战斗力、基层官兵厌战导致最终撤军时。
 # Q&amp;A 环节
-**发言人2**：阿富汗到底有啥好呀？为啥都想打它？
-**发言人1**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-**发言人2**：是不是阿富汗有石油啊？
-**发言人1**：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
-**发言人3**：其实这个我感觉得用当时的冷战思维来看，阿富汗当时被苏联化为苏联大家庭中的一员。根据勃列日涅夫的逻辑，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗是必须要下场的，而阿富汗又是一个非常特殊的战略要地，加上苏联的错判，导致苏联大大的战略性失误。
-**发言人1**：对的，同时期冷战状态也是苏攻美守时期，苏联咄咄逼人地进行意识形态扩张和军事霸权恐吓，共同导致了苏联出兵阿富汗。
-**发言人3**：之前看阿富汗那边把部队叫什么圣战者，这是什么意思？
-**发言人1**：就是狂烈激进的伊斯兰圣战思想，加上从上到下宗教式的洗脑，导致阿富汗圣战者像二战时期日本军国主义荼毒下的日本军民一样，抱着同归于尽的思想进行圣战。
-**发言人3**：这次苏阿战争之前已经有三次英阿战争，阿富汗被称为帝国坟场，为什么这个位置这么难打？
-**发言人1**：这个国家90%都是高原山地地带，是天然的游击战地区。除了喀布尔和坎大哈等主要城市以外，剩下大部分地区都是乡村部落长老制，政府没有任何控制力，各个村落与部落各自为政，导致任何列强和阿富汗城市政府都无法对广大高原山地形成有力控制。同时期咱们国家帮助阿富汗圣战抵抗者，教他们地道战、地雷战等抗战时期的战法；美国也援助了比较先进的单兵武器，比如毒刺防空导弹，可以有效压制苏联最先进的雌鹿武装直升机。坦克和步兵战车在阿富汗无法形成有效战斗力，因为那些装备主要用于平原地带，高原山地还是要靠步兵加武装直升机。苏联军事实力看似庞大，但武器发挥不了作用，基层官兵普遍厌战，士气一落千丈，最终1989年从上到下扛不住压力撤军。
-**发言人2**：咱们男生基本都说完了，都说过一遍了。
-**发言人1**：也是给了一些枪炮，比如咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助形式把咱们国家已经饱和的军工业产业稀释掉，同时也是为了抵抗苏联霸权主义，和西方盟国达成秘而不宣的默契。
-**发言人3**：只提供军火，但是没有派人。
-**发言人1**：专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
+**听众**：阿富汗到底有啥好呀？为啥都想打它？
+**主讲人**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+**听众**：哎，是不是阿富汗有石油啊？
+**主讲人**：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
+**听众**：其实这个我感觉得用当时的冷战思维来看，因为阿富汗当时被苏联化为是苏联势力，就是苏联大家庭中的一员。根据勃列日涅夫的逻辑来说，是不允许任何一个成员外出的。所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，所以加上苏联这个错判，导致苏联大大的战略性失误。
+**主讲人**：对的，同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人地进行意识形态的扩张以及军事霸权的恐吓，然后共同导致了苏联出兵阿富汗。
+**听众**：之前看那个阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
+**主讲人**：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民那样不顾一切、抱着同归于尽的思想进行圣战。
+**听众**：其实这次苏阿战争之前，已经有三次英阿战争，阿富汗被称为帝国坟场，可以简单说一下为什么这个位置这么难打？虽然它的国土面积没有那么大，经济实力又没有那么好。
+**主讲人**：因为这个国家百分之九十都是处于高原山地地带，就是一个天然的游击战地区。除了喀布尔和坎大哈那几个主要城市以外，剩下大部分百分之九十的地区都是乡村部落长老制，政府没有任何控制力，各个村落与部落各自为政，导致任何列强以及阿富汗城市政府都无法对广大高原山地形成有力控制。同时期咱们国家也帮助阿富汗圣战抵抗者，教他们地道战、地雷战这样的战法，和苏联持续进行游击战争。美国同时期也援助了比较先进的单兵武器，比如毒刺防空导弹，可以有效压制苏联最先进的武装直升机雌鹿。坦克和步兵战车在阿富汗没办法形成有效战斗力，因为这些装备主要用在平原地带，在高原山地还是要以步兵加武装直升机才能形成有效战斗力。苏联军事实力看似庞大，但实际上武器发挥不了任何作用，加上基层官兵普遍厌战，士气一落千丈，最终1989年从上到下扛不住压力撤军。
+**听众**：咱们男生基本都说完了，都说过一遍了。
+**主讲人**：也是给了一些枪炮，比如咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助形式把咱们国家已经饱和的军工业产业稀释掉，同时也为了抵抗苏联霸权主义和西方盟国达成了一种秘而不宣的默契。
+**听众**：只提供军火，但是没有派人。
+**主讲人**：专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -17237,67 +17090,67 @@
       <c r="C53" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由发言人2以《白夜行》为引子发起，成员共4人（发言人1、发言人2、发言人3、发言人4），围绕各国文学特点及社会历史背景展开漫谈式交流。讨论由日本文学切入，依次谈及法国、俄国、英国、美国文学，并延伸至国内底层文学、台湾电影《假如我是真的》、历史饥荒与移民原因，最后以《西游记》狮驼岭章节的解读收尾。整体以分享观点为主，未形成统一结论，发言人2多次引导话题并承担主要讲解角色。讨论按议题逐块推进，各成员自由插话补充，涉及《白夜行》《悲惨世界》《变色龙》《命运与生活》《圣诞欢歌》《雾都孤儿》《了不起的盖茨比》《海燕》等作品，以及《菊与刀》《古拉格群岛》等非虚构著作。关键锚点包括：**《古拉格群岛》最早出版法语版、俄语版在苏联解体后发行**；**台湾电影《假如我是真的》拍摄于上世纪七十年代末、八十年代初**；**狮驼岭距灵山约500公里**。
+本次讨论为四人（发言人1、发言人2、发言人3、发言人4）围绕各国文学特点及底层民众描写的自由漫谈，由《白夜行》引出，先后谈及日本、法国、俄国、英国、美国文学，并延伸至《西游记》狮驼岭章节解读及《假如我是真的》等影视作品。讨论以分享观点为主，未形成统一结论，整体呈发散式推进，由发言人2主要引导话题转换。关键锚点包括《菊与刀》、契诃夫、《古拉格群岛》（最早出版法语版，俄语版在苏联解体后发行）、狮驼岭距灵山约500公里等。
 # 发言要点
 ## 日本文学《白夜行》讨论
-- **发言人1**：《白夜行》是悬疑小说，叙事手法独特，上来就隐藏线索，让人一直猜不到真相，每个人都有嫌疑，但**结局非常阴暗**。
-- **发言人2**：美国作家本尼迪克特的《菊与刀》生动描绘了日本人性格特点，从《白夜行》中也能体现出来，并由此引出各国文学偏好问题。
+- **发言人1**：白夜行是悬疑小说，叙事手法独特，上来都是隐藏线索，让人一直猜不到真相，每个人都有嫌疑，但**结局非常阴暗**。
+- **发言人2**：美国作家本尼迪克特《菊与刀》生动描绘日本人性格特点，从《白夜行》中也能体现，并由此引出对各国文学偏好的讨论。
 ## 法国文学特点讨论
-- **发言人2**：雨果的《悲惨世界》体现浪漫的理想主义精神和奉献，是法国文学的代表。
-- **发言人1**：法国文学有抗争精神，因为法国历史上革命很多。
-- **发言人4**：法国小说描绘底层民众较多，而英国小说多是贵族生活。
-- **发言人1**：英国文学想维持贵族形象，法国则因革命多而不同。
-## 俄国文学与底层描写比较
-- **发言人2**：契诃夫作品包括《变色龙》《装在套子里的人》《凡卡》，个人比较喜欢这些。
-- **发言人2**：《古拉格群岛》真正批判了人性黑暗面，**最早出版的是法语版，俄语版要等到苏联解体后才发行**。
-- **发言人2**：格罗斯曼是苏联红军战地记者，著有《命运与生活》，写红军进入欧洲后看似不公的问题，从平民视角看苏联红军基层的真实形象。
-- **发言人1**：国内底层文学如《平凡的世界》写得也很深刻，但很多因政策原因不让看，以前根据底层小说改编的电影也不让看。
-- **发言人2**：俄国文学对人性丑恶的揭露与批判更为讽刺，如列夫·托尔斯泰曾为前线俄军，把百姓疾苦与贵族奢华对比讽刺，因沙俄新闻管制严厉而以小说形式发表。
+- **发言人1**：法国文学有抗争精神，因为法国革命次数多。
+- **发言人4**：法国小说描绘底层民众较多，英国小说多是贵族生活。
+- **发言人2**：法国文学体现浪漫理想主义精神与奉献，在《悲惨世界》中体现得生动。
+## 俄国文学与底层描写
+- **发言人2**：契诃夫作品包括《变色龙》《装在套子里的人》《凡卡》；《古拉格群岛》真正批判人性黑暗面，**最早出版法语版，俄语版要等苏联解体后才发行**。
+- **发言人4**：俄国文学比法国文学曲折，戏剧性更明显。
+- **发言人1**：国内底层文学如《平凡的世界》写得深刻，但因政策原因受限，相关电影也不让看。
 ## 台湾电影《假如我是真的》讨论
-- **发言人2**：台湾电影《假如我是真的》改编自果戈里《钦差大臣》，结合文革知青上山下乡事件，拍摄于**上世纪七十年代末、八十年代初**。
-- **发言人2**：当时台湾与大陆搞舆论宣传战，台湾通过电影批判大陆上山下乡、文革时期的不公。
-- **发言人3**：询问电影内容，发言人2表示主要讲知青上山下乡时期的真实体现，不剧透。
-## 英国文学与移民原因讨论
+- **发言人2**：台湾电影《假如我是真的》改编自俄国果戈里《钦差大臣》故事背景，结合文革知青上山下乡真实事件，是**上世纪七十年代末、八十年代初**台湾与大陆舆论宣传战的产物，通过电影批判大陆上山下乡时期的不公。
+- **发言人1**：台湾拍电影既批判对方也批判自己。
+## 英国文学与移民原因
 - **发言人1**：英国文学如《圣诞欢歌》《雾都孤儿》也讲底层人，描写贵族与穷人之间的鸿沟，穷人把希望寄托在宗教或虚无的东西上。
-- **发言人2**：欧洲土地无法承载人口膨胀，以英国、爱尔兰为主带头移民北美新大陆，这是根本原因。
-## 美国文学特点讨论
-- **发言人2**：美国历史较短，叙事风格不同于欧洲，更多表现在现代社会，与欧洲理想主义精神图腾差别较大。
-- **发言人1**：美国历史太短，美洲大陆没发生欧亚大陆那么多悲惨事件，相对幸福，提及《了不起的盖茨比》。
-- **发言人2**：北美大平原农业资源广阔，**美国到今天经济不好也永远不缺粮食**，从未发生饥荒，美国人无法真正理解饥荒为何物。
-## 历史饥荒与文学关联讨论
+- **发言人2**：欧洲土地无法承载过多人口膨胀，以英国、爱尔兰为主带头移民北美新大陆，这是英国底层移民美国的根本原因。
+## 美国文学特点
+- **发言人2**：美国文学侧重现代社会，与欧洲理想主义精神图腾不同；马克·吐温、海明威的作品零散看过一些。
+- **发言人1**：美国历史短，美洲大陆没发生亚欧大陆那么多悲惨事件，相对幸福；提到《了不起的盖茨比》。
+- **发言人2**：北美大平原农业资源广阔，美国经济不好也永远不缺粮食。
+## 饥荒与历史事件
+- **发言人2**：美国从未发生过饥荒，美国人无法真正理解饥荒为何物；黑死病、天花、旱灾蝗灾等在美国从未发生过。
 - **发言人1**：提及电影《一九四二》讲大饥荒和战乱。
-- **发言人2**：日本人因给灾民发放粮食而占领河南省大部地区，国民党对灾区视而不见。
-- **发言人1**：有人为换取粮食给日军送情报，这是人性，没办法。
-## 高尔基作品讨论
-- **发言人2**：高尔基《海燕》体现老百姓被压迫久了之后的呐喊和奋起反抗，是走投无路后的挣扎。
-- **发言人1**：高尔基作品感觉特别正面，反倒是苏联时期其他作者看得很少。
+- **发言人2**：日本人给灾民发放粮食，国民党对灾区视而不见，结果日本人占领河南省大部地区。
+- **发言人1**：灾民给日军送情报换粮食，这是人性，没办法。
+## 俄国文学与讽刺
+- **发言人2**：列夫·托尔斯泰曾为前线俄军，把老百姓疾苦与贵族奢华进行讽刺对比，因沙俄新闻管制严厉而以小说方式发表；**俄国文学对人性丑恶的揭露与批判比法国更讽刺**。
+- **发言人2**：苏联时期喜欢格罗斯曼，他是红军战地记者，写《命运与生活》以平民视角揭露红军进入欧洲后的不公问题。
+## 高尔基与《海燕》
+- **发言人2**：高尔基《海燕》体现老百姓被压迫久了之后的呐喊与奋起反抗，是走投无路后的挣扎。
+- **发言人1**：高尔基作品正面，苏联时期作者虽多但看得少，反倒是高尔基因正面宣传看得比较多。
 ## 《西游记》狮驼岭章节解读
-- **发言人2**：狮驼岭章节描写佛门三大圣兽青狮、白象、大鹏偷离佛门到下界作妖，把全城人吃掉后扶植小妖当公民，唐僧师徒路过时尸骸遍地，孙悟空都不战而弃。
-- **发言人2**：原著描写人皮当地毯、骷髅头骨当装饰物和器具，**此地距离灵山不过500公里**，却发生如此人伦惨剧，与佛教普度众生、众生平等理念大相径庭。
-- **发言人2**：吴承恩在古代就预测并批判揭露佛教被上层王公大臣用来迷惑底层民众、进行高压奴役统治，并联系旧社会西藏与印度菩提迦耶距离不过数百公里也有类似惨剧。
-- **发言人2**：如果共产党没有解放西藏，这样的悲剧会延续到今天，这也是汉传佛教与藏传佛教截然不同的本质。
-- **发言人1**：黑神话悟空没有设计狮驼岭那一章，估计不太好设计，太血腥不好过审，且意义深刻，剧情既要委婉又要深刻很难。
-- **发言人2**：狮驼岭章节中如果不是佛祖出手，孙悟空终究要被大鹏精打败，大鹏精是**整个《西游记》里唯一能遛猴子的反派角色**。
+- **发言人2**：狮驼岭章节中三大魔头青狮、白象、大鹏吃光城池居民，扶植小妖成为国家公民，孙悟空不战而弃、浑身发抖，满国尸骸遍地。
+- **发言人2**：狮驼岭**距离灵山仅约500公里**却发生人伦惨剧，与佛门普度众生、众生平等大相径庭；吴承恩借此批判佛教被上层王公大臣用来迷惑底层民众、进行高压奴役统治。
+- **发言人2**：电视剧未把狮驼岭惨状拍得生动，人皮当地毯、骷髅头骨当装饰物等细节未呈现；并联系旧社会西藏、印度菩提迦耶附近同样惨剧，称共产党解放西藏终结了这种悲剧。
+- **发言人1**：游戏《黑神话悟空》没有设计狮驼岭章节，因太血腥不好过审，且剧情既要委婉又要深刻，很难设计。
+- **发言人2**：狮驼岭章节中若非佛祖出手，孙悟空终将被大鹏精打败，大鹏精是**全剧中唯一能遛猴子的反派角色**。
 # 共识形成
-- **一致意见**：与会者普遍认同各国文学与其社会历史背景紧密相关，文学常反映底层民众生活与社会矛盾。发言人1、发言人2、发言人4均认可法国文学多描绘底层民众、英国文学多聚焦贵族生活，而俄国文学对人性丑恶的揭露与批判更为讽刺。
-- **倾向性认识**：发言人2提出美国因北美大平原农业资源丰富、历史上未发生大饥荒，故美国人难以真正理解饥荒；发言人1对此表示认同，并补充亚欧大陆曾经历瘟疫、大饥荒等灾难。发言人2还指出欧洲土地无法承载人口膨胀，以英国、爱尔兰为主移民北美，与会者未提出异议。
-- **主要分歧点**：在比较法国与俄国文学对底层民众的描写时，发言人2倾向认为俄国文学更为生动、讽刺性更强；发言人4则认为俄国文学戏剧性更明显，但未明确表态孰优。发言人1提出国内底层文学（如《平凡的世界》）同样深刻，但因政策原因受限，发言人2未直接回应，转而介绍台湾电影《假如我是真的》作为对照，双方未就此达成统一结论。
-- **关键口径**：发言人2指出《古拉格群岛》最早出版法语版，俄语版在苏联解体后才发行；狮驼岭距灵山约500公里，原著描写佛门三大圣兽吃人、尸骸遍地，与佛教「普度众生」理念相悖。
+- **一致意见**：与会者普遍认同各国文学均以不同方式反映底层民众生活，且文学风格与各国历史、社会现实密切相关。发言人2与发言人1、发言人4在法国文学具有抗争精神、英国文学多描写贵族生活但《圣诞欢歌》《雾都孤儿》等也涉及底层、俄国文学对人性丑恶的揭露与批判比法国更讽刺等判断上形成共识。
+- **倾向性认识**：发言人2提出美国文学侧重现代社会、与欧洲理想主义不同，因美洲大陆未经历亚欧大陆的饥荒瘟疫等灾难，美国人无法真正理解饥荒为何物；发言人1对此表示认同，认为美国相对幸福。发言人1指出国内底层文学如《平凡的世界》写得深刻，但因政策原因受限，发言人2未直接反驳，转而介绍台湾电影《假如我是真的》作为对照。
+- **主要分歧点**：发言人1认为英国文学描写底层民众较多（如《圣诞欢歌》《雾都孤儿》），发言人2未直接回应此点，而是转向解释欧洲人口膨胀导致移民北美，双方对英国文学底层描写的侧重程度未展开深入交锋。发言人2对《西游记》狮驼岭章节的解读（批判佛教被上层利用迷惑底层民众）为个人观点，发言人1仅回应游戏《黑神话悟空》未设计该章节因血腥和过审难，未对解读本身表示赞同或反对。
 # 待探讨问题与后续
-- **未确认**：发言人2在讨论《古拉格群岛》时，将作者表述为「托斯托耶夫斯基」，并称该书最早出版的是法语版、俄语版在苏联解体后才发行；该说法与通常认知存在出入，现场无人核实或纠正。
-- **未确认**：发言人2称台湾电影《假如我是真的》改编自俄国作家果戈里的《钦差大臣》，并结合文革知青上山下乡事件拍摄于上世纪七十年代末、八十年代初；该片与原著的具体对应关系未在讨论中展开核实。
-- **未定论**：发言人1提出国内底层文学（如《平凡的世界》）「写得挺深刻」，但因政策原因「不让你看了」，且相关电影也受限；发言人2未直接回应，该话题被搁置，未进一步讨论具体作品与限制依据。
-- **未定论**：发言人2解读《西游记》狮驼岭章节时，将书中描写与旧社会西藏、藏传佛教直接关联，并称「汉传佛教和藏传佛教的根本本质截然不同」；发言人1仅表示「确实挺吓人」，未对该论断表示认同或反对，分歧未展开。
-- **未确认**：发言人2称「日本人给灾民发放粮食，国民党对灾区视而不见，导致日本人占领河南省大部地区」；该历史叙述未在讨论中验证，发言人1仅以「人性」回应，未作核实。
-- **未定论**：发言人2提出「欧洲土地无法承载人口膨胀，以英国、爱尔兰为主移民北美」作为英国底层文学背景的延伸解释；发言人1未回应，该因果关联未被进一步讨论。</t>
+- **未确认**：发言人2提到《古拉格群岛》的作者为「托斯托耶夫斯基」，但该作品实际作者为索尔仁尼琴，发言中未就此澄清，需核实作者归属。
+- **待核实**：发言人2称《古拉格群岛》最早出版版本为法语版，俄语版在苏联解体后才发行，该出版时间线未在讨论中进一步验证。
+- **未定论**：发言人1认为国内底层文学（如《平凡的世界》）写得深刻，但因政策原因受限，发言人2未直接回应，双方对国内底层文学受限程度的看法未达成一致。
+- **未确认**：发言人2解读《西游记》狮驼岭章节时，称「此地距离灵山也不过500公里左右」，该距离数据出自原著还是个人推算，讨论中未说明。
+- **未定论**：发言人2将狮驼岭章节联系西藏历史，称「描绘了旧社会时期的西藏」，发言人1仅回应「确实挺吓人」，未对该历史关联性展开讨论或表态。
+- **待核实**：发言人2提及电影《假如我是真的》改编自俄国小说并结合文革真实事件，但未指明具体改编自哪部俄国小说，仅提到结合果戈里《钦差大臣》的故事背景，需进一步核实改编来源。
+- **未确认**：发言人2称「日本人给灾民发放粮食，而国民党对灾区视而不见，导致日本人占领河南省大部」，该历史叙述未在讨论中提供史料依据，需核实。
+- **未定论**：发言人1提到游戏《黑神话悟空》未设计狮驼岭章节，因「太血腥、不太好过审」，发言人2回应「设计出来不太好」，但未讨论游戏方是否曾计划设计该章节，属推测性话题。</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>55.1</v>
+        <v>49.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5886/3309</t>
+          <t>5886/3092</t>
         </is>
       </c>
     </row>
@@ -17370,82 +17223,72 @@
       <c r="C54" t="inlineStr">
         <is>
           <t># 全文摘要
-本次团队例会由主持人（发言人1）召集，产品经理（发言人2）、开发1（发言人3）、开发2（发言人4）参与，围绕手机图库项目的进展、排期与风险进行对齐。会议覆盖智能分类与相册推荐改版、AI智能标签接口与模型部署、云相册同步与内存管理、缩略图渲染优化、端侧预过滤、时间轴加载优化、AI修图功能预留及项目排期等板块。
-会议确认多项技术方案与排期：AI识别采用本地缓存策略，开发1预计**三天**联调完；端侧预过滤方案被采纳，需申请**两百兆**本地缓存空间，按需加载预计**两天**搞定；云相册同步采用分片加载（每次拉**五十张**）；缩略图渲染通过JPEG硬解换软解，内存占用降**30%**，主流三款车型灰度帧率稳定**60帧**、低端机**50帧**。最终决定月底封版，内测包暂定下周三发，周四性能压测需拿达标数据。
+本次团队例会由主持人召集，产品经理、开发1、开发2等四方参与，围绕手机图库项目进展、排期与风险对齐展开。会议覆盖产品交互迭代、AI智能标签、云同步、缩略图渲染、时间轴加载、AI修图预留及内测计划等议题。关键结论包括：隐私相册入口提升至首部顶部二级菜单；AI识别采用本地缓存策略；云同步采用分片加载；时间轴加本地索引预加载；AI修图预留接口并做插件化架构。里程碑按原定计划月底封版，内测包暂定下周三发。关键数字：AI识别模型准确率提升约88%，单次请求耗时从800毫秒涨至约1.5秒，缩略图渲染内存占用降约30%，主流机型帧率稳定60帧，管线重构工作量多出一周。
 # 分段速览
-## 00:00:00-00:01:23 开场与产品侧汇报
-主持人开场说明会议目的为对齐手机图库项目进展、排期与风险，先由产品侧同步。产品经理汇报智能分类和相册推荐改版进展，高保真原型已出V1.5版，调整了网格视图交互逻辑并增加长按微动效反馈；同时反馈低端机上滑列表偶发掉帧、隐私相册入口过深两个问题，建议将入口提到首部顶部二级菜单。
-## 00:01:23-00:03:19 AI识别模型与本地缓存方案
-主持人确认隐私相册入口调整可行，要求产品出交互方案评审，并催促掉帧问题需在性能压测前解决。开发1汇报后端V2识别模型已跑通，准确率提升约88%，但视频帧提取功能使单次请求耗时从800毫秒涨至1.5秒。产品经理否决异步推送方案，提出本地缓存策略，开发1确认可行并计划下午拉分支，预计三天联调完。
-## 00:03:19-00:05:03 同步模块与缩略图渲染优化
-开发1提出云相册断点续传在弱网下状态机紊乱，开发2反馈同步队列积压超一千张时部分机型OOM崩溃，已采用分片加载机制每次拉五十张，但拖慢同步进度。主持人确认后台静默同步权限审核严、大概率下不了，按分片方案走。开发2汇报缩略图渲染优化：JPEG硬解换软解后内存占用降约30%，主流三款车型灰度帧率稳定60帧、低端机50帧；另发现批量删除照片时数据库偶发锁死，已用消息队列临时规避。
-## 00:05:03-00:07:01 端侧预过滤与时间轴预加载
-主持人提出端侧轻量级模型预过滤方案，可平均压一半耗时。开发1评估需申请两百兆本地缓存空间，产品经理建议按需加载，开发1确认用现有资源下发模块、约两天搞定。开发1另汇报时间轴视图滑动到老照片时卡死三秒以上，根因是EXIF解析耗时和磁盘IO瓶颈，计划加本地索引预加载，最近三个月照片建树状结构、滑到底部动态加载旧数据。
-## 00:07:01-00:09:42 资源冲突确认与AI修图预留
-开发2确认预加载放主线程IO池、同步放子线程后台服务，互不冲突，但需用户授权媒体和存储权限，产品经理明天出引导弹窗稿。运营提出下版本加AI修图快捷入口，主持人决定本次不硬塞，在PRD预留接口和UI占位，开发侧做插件化架构；开发2提出重构图片处理管线、用GLSL写统一接口，工作量约多一周，需调整优先级。
+## 00:00:00-00:01:22 开场与产品交互迭代
+主持人开场说明会议目的为对齐手机图库项目进展、排期与风险，先由产品侧汇报。产品侧同步智能分类和相册推荐改版进展，高保真原型已出V1.5版，调整网格视图交互逻辑并给长按手势增加微动效反馈。测试反馈低端机上滑列表偶尔掉帧，已与开发2沟通拟通过降低预览图缩放级别换帧。用户调研收到隐私相册入口太深的吐槽，建议将入口提到首部顶部二级菜单，主持人认为不算大改动，要求产品出交互方案供评审，并强调掉帧问题需抓紧，下周将进入性能压测。
+## 00:01:23-00:03:18 AI智能标签接口与模型部署
+开发1汇报后端V2识别模型已跑起来，准确率较上一代提升约88%，但因新增视频帧提取功能，单次请求耗时从八百毫秒涨至约一点五秒，询问产品侧接受度，提出可改异步推送。产品否决异步推送，认为用户会觉功能卡死，建议先做本地缓存策略——首次识别慢、之后本地读库秒出。开发1确认可行，计划下午拉分支改逻辑，预计三天联调完，但提示缓存命中率低时需回溯。开发1另提及云同步断点续传在弱网下出现状态机紊乱，询问开发2是否遇到类似问题。
+## 00:03:19-00:05:02 云同步内存管理与缩略图渲染优化
+开发2反馈同步队列积压到一千张以上时部分机型出现OOM崩溃，尤其iOS内存回收机制激进，已加装分片加载机制每次只拉五十张，但拖慢同步进度，建议加后台静默同步权限或允许用户手动设置同步频率。主持人表示后台同步权限审核严、大概率下不了，先按分片加载方案走但进度不能拖。开发2汇报缩略图渲染优化进展，用新图片解码库将JPEG硬解换软解，内存占用降约30%但CPU占用上升，已在主流三款机型灰度，帧率稳定六十帧、低端机约五十帧，周四性能报告今晚出初稿。
+另提及批量删除照片时若同时触发回收站重建索引，数据库偶尔锁死，已用消息队列排队临时规避，正式修复排到下下周版本。
+## 00:05:03-00:07:00 端侧预过滤与时间轴加载优化
+主持人建议开发1在端侧做初步筛选，用轻量级模型先过滤非图片内容再走全量云端识别，可平均压下一半耗时。开发1认可思路，将评估模型体积和端侧推理开销，可能需再申请两百兆本地缓存空间。产品表示安装包加两三百兆问题不大，建议做成按需加载，用户首次进智能标签时才触发下载。开发1确认可用现有资源下发模块，约两天搞定，并拉开发2配合端侧推理联调。开发1另提出时间轴视图滑动到二十年前老照片时页面卡死三秒以上，原因是历史图片EXIF解析耗时太长加磁盘IO瓶颈，计划加本地索引预加载，最近三个月照片建树状结构，滑到底部再动态加载旧数据。
+## 00:07:01-00:09:41 资源冲突确认与AI修图预留
+主持人同意时间轴预加载改动，但提醒别与云同步模块抢资源。开发2确认不冲突，预加载放主线程IO池、同步放子线程后台服务，但需用户授权媒体和存储权限，建议设计引导弹窗，产品表示明天出稿、走柔和提示路线。产品提出运营希望下版本加AI修图快捷入口，本次主线是性能和分类、硬塞风险大，建议PRD先写接口逻辑和UI占位，开发侧做成插件化架构。开发1确认后端可做标准RESTful加Swogger文档，开发2提出需重构图片处理管线，建议把渲染层抽成插件化、用GLSL写统一接口，工作量多出一周左右，需确认能否把非核心Bug修复往后挪。
 ## 00:09:42-00:12:18 排期确认与收尾
-主持人调整优先级，非核心UI微调往后排，要求开发2下班前评估管线重构工作量、开发1排联调时间赶在周五前跑通主干流程，周四性能压测需拿达标数据。确认月底封版、内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块。开发1需今晚搭好接口联调环境并拉群与DBA对齐索引策略，开发2今晚继续跑压测数据；性能报告分开列iOS和安卓对比数据，由测试组合并成一份总览。
+主持人调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化，要求开发2今天下班前评估精确工作量，开发1排联调时间尽量周五前跑通主干流程，周四性能压测由测试部配合拿达标数据。产品确认下午定稿隐私相册入口和引导弹窗稿子、明天上午拉UI走查，并制作AI修图占位图。里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块。开发1提出需与数据库组对齐索引策略，主持人让其拉群由DBA配合优化建表。开发2建议性能报告将iOS和安卓对比数据分开列，主持人同意并让测试组合并成一份总览，产品UI走查下午两点参加、稿子十一点半前发。
 # 要点梳理
-## 智能分类与相册推荐改版
-- **高保真原型**：已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈
-- **掉帧问题**：测试反馈低端机上滑列表偶尔掉帧，已与开发2沟通，拟通过降低预览图缩放级别换帧
-- **隐私相册入口**：用户调研反馈入口太深，建议提到首部顶部二级菜单；产品经理确认不算大改动，由产品出交互方案评审
+## 产品交互迭代与用户反馈
+- **原型进展**：高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈。
+- **掉帧问题**：测试反馈部分低端机上滑列表偶尔掉帧，产品已与开发2沟通，拟通过降低预览图缩放级别换帧。
+- **隐私相册入口**：用户调研反馈入口太深，建议提到首部顶部二级菜单；主持人确认不算大改动，产品出交互方案供评审。
 ## AI智能标签接口与模型部署
-- **识别模型**：后端V2版已跑通，准确率较上一代提升约88%
-- **请求耗时**：因新增视频帧提取功能，单次请求耗时从800毫秒涨至约1.5秒
-- **方案取舍**：异步推送方案被产品否决（用户无实时结果会觉功能卡死）；改为本地缓存策略，首次识别慢、之后本地读库秒出
-- **实现排期**：开发1下午拉分支改逻辑，预计三天联调完；缓存命中率低时需回溯，产品需心里有底
-## 云相册同步与内存管理
-- **断点续传**：弱网环境下状态机紊乱，开发2确认有类似问题
-- **OOM崩溃**：同步队列积压超一千张时部分机型崩溃，iOS内存回收机制较激进
-- **分片加载**：每次只拉五十张，处理完再拉下一批；会拖慢同步进度
-- **后台权限**：后台静默同步权限审核严，大概率下不了；产品经理拍板按分片加载方案走，进度不能拖
-## 缩略图渲染优化
-- **解码方案**：JPEG硬解换软解，内存占用降约30%，CPU占用上升
-- **灰度数据**：主流三款机型帧率稳定60帧，低端机约50帧；周四性能报告初稿今晚出
-- **数据库锁死**：批量删除照片同时触发回收站重建索引时偶发锁死；临时规避用消息队列排队，正式修复排进V1.2迭代
-## 端侧预过滤与按需加载
-- **预过滤方案**：端侧轻量级模型先扫一遍，过滤gif或截图，再走全量云端识别，平均可压一半耗时
-- **资源申请**：端侧推理需再申请两百兆本地缓存空间；产品确认安装包加两三百兆问题不大
-- **按需加载**：用户首次进图库智能标签时才触发下载，用现有资源下发模块，约两天搞定；开发1拉开发2配合端侧推理联调
+- **模型升级**：后端V2识别模型已跑通，准确率较上一代提升约88%。
+- **耗时增加**：新增视频帧提取功能后，单次请求耗时从800毫秒涨至约1.5秒；异步推送方案被产品否决。
+- **本地缓存策略**：开发1确认可行，下午拉分支改逻辑，预计三天联调完；缓存命中率低时需回溯，产品需心里有底。
+- **端侧预过滤**：主持人建议先用轻量级模型过滤gif或截图，再走全量云端识别，可平均压下一半耗时；开发1评估模型体积和端侧推理开销，可能需申请200兆本地缓存空间。
+- **按需加载**：产品建议首次进图库智能标签时才触发下载，开发1确认用现有资源下发模块即可，约两天搞定。
+## 云同步与内存管理
+- **断点续传问题**：弱网环境下状态机紊乱，开发2确认有类似问题。
+- **OOM崩溃**：同步队列积压到一千张以上时部分机型崩溃，iOS内存回收机制较激进。
+- **分片加载方案**：每次只拉五十张，处理完再拉下一批；后台静默同步权限审核严、大概率下不了，按分片方案走但进度不能拖。
+## 缩略图渲染优化与性能压测
+- **解码库替换**：JPEG硬解换软解，内存占用降约30%，CPU占用上升。
+- **灰度数据**：主流三款机型帧率稳定60帧，低端机约50帧；周四性能报告今晚出初稿。
+- **数据库锁死Bug**：批量删除照片同时触发回收站重建索引时数据库偶尔锁死，临时用消息队列规避，正式修复排进V1.2迭代。
 ## 时间轴视图加载优化
-- **卡死Bug**：滑动到二十年前老照片时页面卡死三秒以上，测试提了三个优高优Bug
-- **根因**：历史图片EXIF解析耗时太长，叠加磁盘IO瓶颈
-- **预加载方案**：最近三个月照片建树状结构，滑到底部动态加载旧数据；预加载放主线程IO池，同步放子线程后台服务，互不冲突
-- **权限引导**：预加载需用户授权媒体和存储权限，产品明天出引导弹窗稿，走柔和提示路线
-## AI修图功能预留
-- **需求来源**：运营希望下个版本加AI修图快捷入口（一键去背景、智能调色等）
-- **范围决策**：本次主线是性能和分类，硬塞风险太大；在PRD里写好接口逻辑和UI占位，开发侧做成插件化架构
-- **管线重构**：开发2提出渲染层抽成插件化，用GLSL写统一接口，工作量多一周；非核心UI微调往后排，资源给到管线重构和AI标签优化
+- **卡顿问题**：滑动到二十年前老照片时页面卡死三秒以上，测试提了三个优高优Bug；根因是历史图片EXIF解析耗时太长加磁盘IO瓶颈。
+- **预加载方案**：最近三个月照片建树状结构，滑到底部动态加载旧数据；预加载放主线程IO池，同步放子线程后台服务，不冲突。
+- **权限引导**：预加载需用户授权媒体和存储权限，产品明天出引导弹窗稿，走柔和提示路线。
+## AI修图功能预留与插件化架构
+- **需求预留**：运营希望下版本加AI修图快捷入口，本次主线是性能和分类、硬塞风险大；PRD先写接口逻辑和UI占位，开发侧做成插件化架构。
+- **后端接口**：做成标准RESTful加Swogger文档，方便后续迭代对接。
+- **渲染管线重构**：开发2建议把渲染层抽成插件化、用GLSL写统一接口，工作量多出一周左右；非核心UI微调往后排，资源给到管线重构和AI标签优化。
+## 项目里程碑与内测计划
+- **排期确认**：里程碑按原定计划月底封版，内测包暂定下周三发。
+- **内测安排**：拉体验官群重点跑AI分类和同步模块，产品做好反馈收集表，开发准备日志抓取。
 ## 结论与决定
-- **隐私相册入口**：提到首部顶部二级菜单，产品出交互方案评审
-- **AI识别方案**：采用本地缓存策略，开发1下午拉分支，预计三天联调完
-- **云相册同步**：按分片加载方案走（每次五十张），进度不能拖
-- **数据库锁死**：临时规避用消息队列排队，正式修复排进V1.2迭代
-- **端侧预过滤**：方案采纳，需申请两百兆本地缓存空间，按需加载用现有资源下发模块，约两天搞定
-- **时间轴预加载**：方案采纳，最近三个月照片建树状结构，滑到底部动态加载旧数据
-- **AI修图**：预留接口和UI占位，开发侧做插件化架构，下次迭代接入
-- **排期**：月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块
+- **方案拍板**：隐私相册入口提升至首部顶部二级菜单；AI识别采用本地缓存策略加端侧预过滤；云同步按分片加载每次五十张；时间轴加本地索引预加载；AI修图预留接口、渲染层插件化。
+- **Bug处理**：批量删除照片数据库锁死，临时用消息队列规避，正式修复排进V1.2迭代。
+- **排期确认**：月底封版、下周三发内测包；周四性能压测需拿达标数据，否则下周过评审会过不去。
 ## 行动项与分工
-- **产品经理（发言人2）**：下午定稿隐私相册入口和引导弹窗稿，明天上午拉UI走查；制作AI修图占位图；十一点半前将UI走查稿发给产品经理（发言人1）
-- **开发1（发言人3）**：下午拉分支实现本地缓存策略，预计三天联调完；今晚搭好接口联调环境，明天与测试过一遍；排模型部署和端侧预过滤联调时间，尽量赶在周五前跑通主干流程；拉群与DBA对齐索引策略
-- **开发2（发言人4）**：今晚继续跑分片加载和渲染优化压测数据，明天同步；评估管线重构精确工作量，今天下班前发产品经理；让测试组把iOS和安卓性能报告合并成一份总览
-- **测试部**：周四配合性能压测，需拿达标数据；性能报告分开列iOS和安卓对比数据
+- **产品经理**：下午定稿隐私相册入口和引导弹窗稿子，十一点半前发主持人；明天上午拉UI走查；制作AI修图占位图；做好内测反馈收集表。
+- **开发1**：下午拉分支改本地缓存逻辑，预计三天联调完；评估端侧预过滤模型体积和推理开销；排联调时间，尽量周五前跑通主干流程；今晚搭好接口联调环境，明天与测试过一遍；拉群与DBA对齐索引策略。
+- **开发2**：评估管线重构精确工作量，今天下班前发产品经理；今晚继续跑分片加载和渲染优化压测数据，明天同步；配合测试组把iOS和安卓性能报告合并成一份总览。
+- **测试组**：周四配合性能压测；把两份性能报告合并成一份总览。
 ## 待确认与风险
-- **缓存命中率**：本地缓存命中率低时需回溯，产品需心里有底
-- **后台权限**：后台静默同步权限审核严，大概率下不了；用户手动设置同步频率是否允许待与产品商量
-- **权限引导**：预加载需用户授权媒体和存储权限，用户可能拒绝，引导弹窗交互设计产品明天出稿
-- **管线重构**：工作量多一周，需调整优先级，精确工作量开发2今天下班前评估
-- **性能压测**：周四需达标数据，否则下周评审过不去
-- **弱网同步**：断点续传状态机紊乱、同步队列积压超一千张时OOM崩溃，分片加载拖慢同步进度</t>
+- **待评估**：端侧预过滤模型体积和端侧推理开销；按需加载对安装包体积的影响；管线重构精确工作量待开发2下班前反馈。
+- **待确认**：后台静默同步权限申请可行性；用户手动设置同步频率是否允许；AI修图功能具体接入时间。
+- **风险信号**：AI识别单次请求耗时1.5秒用户可能等不了；缓存命中率低时需回溯；弱网断点续传状态机紊乱；同步队列积压超一千张时OOM崩溃；分片加载拖慢同步进度；CPU占用上升；时间轴老照片卡死三秒以上；预加载与云同步抢资源；用户拒绝授权媒体和存储权限；管线重构增加一周工作量可能影响其他任务。</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>73.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3605/3720</t>
+          <t>3605/4103</t>
         </is>
       </c>
     </row>
@@ -17532,101 +17375,84 @@
       <c r="C55" t="inlineStr">
         <is>
           <t># 全文摘要
-本次月度研讨会由总监主持，组长、销冠、销售A、销售B等案场团队成员参会，围绕上月销售数据复盘、转化率提升及下月去化目标展开。上月案场总到访320组，环比增加15%，成交76套，转化率23%，较上月27%下降4个百分点；渠道带看占比65%，自然来访35%，蓄客量约3200组，认购到成交流失率约18%。整体量够，但卡在逼定和转化环节。
-针对转化率下降，会议确认多项核心动作：工地开放日标准化，定于每周三下午固定开放，提前两天在CRM系统推送意向客户；逼定权益可视化，替换旧版物料，本周出新版；渠道带看实名制，必须有明确需求标签，否则扣减渠道积分；周末业主答谢会联动去化，统一邀约话术为“老业主专属品鉴宴”，财务和法务周六日轮流值班；本周安排两次专项演练（竞品对比与抗性化解、逼定时机与谈判心理学），每人必须参加，课后现场抽考；销控必须实时同步，CRM系统同步锁房，再出现丢单或客诉直接问责。
-下月集团指标总去化120套，比上月多50%，拆分方案为：销冠28套，组长+销售A+销售B共50套，机动和渠道攻坚储备12套。销售A手头有15个准客户，销售B计划周末搞小型业主答谢会，销冠协助盯两桌。总监要求组长散会后半小时内将会议纪要和任务分解表发到工作群，销冠下周晨会分享逼定案例。
+本次月度研讨会由总监主持，组长、销冠、销售A、销售B共五人参加，围绕上月市场波动下的项目数据复盘与下月去化目标制定展开。会议覆盖上月数据复盘、工地开放日标准化、价格抗性与逼定策略、跟进节奏与渠道带看质量、老带新政策与业主答谢会、下月目标与任务拆分、专项培训与销控纪律、周末答谢会细节与配套等议题。会议确认五项核心动作：工地开放日每周三固定开放、逼定权益可视化并更新物料、渠道带看实名制与质量考核、周末业主答谢会联动去化、专项培训与销控纪律。上月案场总到访320组，环比增加15%达标，但成交76套、转化率23%，较上月27%下降4个百分点；下月集团指标总去化120套，比上月多50%，拆分销冠28套、组长与销售A及销售B共50套、剩余12套机动。
 # 分段速览
-## 00:00:00-00:01:17 开场与整体数据复盘
-总监宣布月度研讨会定于下午两点至两点四十，共四十分钟，指出上月市场波动大、项目整体去化尚可但部分数据不理想。组长汇报后台完整数据：案场总到访三百二十组，环比增百分之十五，达标；成交七十六套，转化率百分之二十三，较上月百分之二十七下降；渠道带看占比百分之六十五，自然来访百分之三十五；蓄客量约三千二百组，认购到成交流失率约百分之十八。总监总结为量够但卡在逼定和转化环节，并指出渠道带看比例过高反映自主拓客与案场拦截能力退化。
+## 00:00:00-00:01:17 开场与数据复盘
+总监宣布会议定在下午两点到两点四十，共四十分钟，要求内容扎实。组长汇报上月完整数据：案场总到访三百二十组，环比增加百分之十五，达标；但成交七十六套，转化率百分之二十三，比上月百分之二十七下降。渠道带看占比百分之六十五，自然来访百分之三十五，蓄客量约三千二百组，认购到成交流失率约百分之十八。总监定性为量够但转化不足，指出渠道占比过高意味着自主拓客和案场拦截能力退化。
 ## 00:01:53-00:03:36 客户流失抗性分析
-销冠复盘上月流失客户，归纳两大抗性：价格预期上竞品推特价房、首付分期或送物业费，客户心理有落差；交付信心上客户细问园林选材、车库层高、外墙保温层，怕买错，建议把工地实时进展和材料样板直接呈现。销售A补充改善型夫妻档案例，三次带看均请施工经理陪同，客户因工程透明才成交，但工地开放日频率不够、陪看占时间影响转化。组长反馈置业顾问反映开放日流程繁琐、报备审批要半天，建议每周三下午固定开放、提前预告、客户直接对接专属顾问。总监认可，要求组长出标准化方案，定每周三、提前两天在CRM系统推送意向客户。
-## 00:04:22-00:06:12 价格抗性应对与逼定策略
-销冠介绍算总账逼定法：不直接降价，而是拉物业费、车位管理费、装修损耗对比竞品，说明单价虽高两千但十年省物业和维修费，再递限时权益逼定函，本周定可申请多送三年物业费，改善型客户看重确定性。销售B指出客户对限时权益不买账，建议把权益具象化，如打印三年缴费明细放合同旁，同时反映案场物料更新慢、逼定函常是上月版本。组长记下物料问题，联系设计本周出新版，下月搞权益可视化台卡放洽谈区，并指出跟进节奏慢、客户晚上问政策回复慢导致热度下降。总监强调客户不过夜，安排分片包干回访。
-## 00:07:13-00:09:10 渠道带看质量与老带新推进
-总监要求组长带销售A和销售B回访上周未成交的三百多组客户，销冠梳理手头二十几个高意向客户周末逼定；渠道带看下月起必须实名登记并有明确需求标签，否则扣减渠道积分。销售A反映中介抵触查实名，怕渠道不愿推盘，总监表示亲自与渠道部沟通，质量大于数量底线不破。销售B汇报老带新奖励政策已下：成功一套奖两万现金或等值车位券，本月推四组、两组在谈，老业主需话术和礼品支持。组长准备定制伴手礼（高端茶叶礼盒、定制保温杯），销冠建议搞业主推荐官活动，成功推荐可升级物业服务等级（优先预约维修、免费家政清洗一次），总监要求组长下周前出详细执行表。
-## 00:09:46-00:11:20 下月目标拆分与表态
-总监宣布集团下月指标总去化一百二十套，比上月多百分之五十。组长按人员配置和上月产出权重拆分：销冠二十八套，组长与销售A、销售B三人一组共五十套，剩余十二套作机动和渠道攻坚储备。销售A表态能扛，手头十五个准客户等下周认筹通知，希望渠道带看质量再筛一筛；销售B计划周末搞小型业主答谢会，邀请成交业主分享并推老带新政策。销冠支持并协助盯两桌，指出客群与改善型客户重合度高，可联动把高意向客户集中去化。
-## 00:11:20-00:13:08 培训安排与销控纪律
-总监安排周末答谢会分工：销冠带人协助、销售B主抓流程、销售A负责客户邀约和逼定记录。本周安排两次专项演练——竞品对比与抗性化解、逼定时机与谈判心理学，每人必须参加，课后现场抽考，过不了加练，组长盯进度并安排签到考核表挂钩下周绩效系数。组长提出销控表更新延迟、客户定后销售仍推同套房易引客诉，总监定为底线问题，要求销控实时同步、CRM系统同步锁房，再出现丢单或客诉直接问责，组长设专人每小时刷新销控大屏。组长总结五大核心议题：工地开放日优化、逼定权益可视化、渠道带看实名制、周末答谢会联动、专项培训与销控纪律。
-## 00:13:27-00:15:07 细节补充与散会
-销售A建议周末答谢会邀约话术统一为老业主专属品鉴宴，避开促销字眼，销售B随即去改邀约短信和电话模板。销冠补充逼定时财务和法务最好在洽谈区待命，现场签当场出数出收据，客户安全感强，成交率能提至少两成。总监协调财务和法务周六日轮流值班在案场外围，把服务做前置。总监布置会后动作：组长半小时内发会议纪要和任务分解表到工作群，销冠下周晨会分享逼定案例，销售A、销售B盯周末答谢会，总监本人盯渠道和工程对接，随后散会。
+销冠复盘流失客户，指出两大抗性：价格预期方面竞品推特价房、首付分期、送物业费，客户心理有落差；交付信心方面客户细问园林选材、车库层高、外墙保温层，怕买错。销售A补充案例，一对改善型夫妻因工程透明才定房，但工地开放日频率不够、陪看占时间。组长反馈置业顾问反映开放日流程繁琐、报备审批要半天，建议每周三下午固定开放、提前预告、直接对接专属顾问。总监认可，要求组长出标准化方案，提前两天在CRM系统推送意向客户。
+## 00:04:22-00:06:12 逼定策略与物料更新
+销冠分享逼定手法：不直接降价，而是算总账，把物业费、车位管理费、装修损耗拉表对比竞品，说明单价虽高两千但十年省物业和维修费，再递限时权益逼定函，承诺本周定可申请多送三年物业费。销售B指出客户对限时权益不买账，建议把权益具象化，如打印三年缴费明细放在合同旁；同时反映案场物料更新慢，逼定函常是上月版本。组长记录物料问题，联系设计本周出新版，并计划下月搞权益可视化台卡；另指出跟进节奏慢，客户晚上问政策回复慢热度下降。
+## 00:06:12-00:09:10 跟进提速与渠道管控
+总监强调客户不过夜，安排分片包干：组长带销售A和销售B回访上周未成交的三百多组客户，重点盯再考虑考虑的；销冠梳理二十几个高意向客户周末逼定。渠道方面，无效带看多、中介凑数，下月起带看必须实名登记并有明确需求标签，否则扣减渠道积分。销售A担心渠道抵触，总监表示亲自与渠道部沟通，质量大于数量底线不能破。老带新政策已下来，成功一套奖励两万现金或等值车位券，销售B本月推四组、两组在谈；组长准备定制伴手礼，销冠建议搞业主推荐官活动，成功推荐可升级物业服务等级。
+## 00:09:10-00:11:20 下月目标与任务拆分
+总监传达集团指标：下月总去化一百二十套，比上月多百分之五十。组长按人员配置和上月产出权重拆分：销冠二十八套，组长加销售A、销售B共五十套，剩余十二套作为机动和渠道攻坚储备。销售A表态手头有十五个准客户等下周认筹通知，五十套盘子能扛住，但希望渠道带看质量再筛一筛；销售B计划周末搞小型业主答谢会，邀请成交业主分享推老带新政策。销冠支持联动，客群重合度高，可把高意向客户拢到一起周末集中去化。
+## 00:11:20-00:15:07 培训、销控纪律与收尾
+总监安排周末答谢会分工：销冠带人协助、销售B主抓流程、销售A负责客户邀约和逼定记录。本周安排两次专项演练，竞品对比与抗性化解、逼定时机与谈判心理学，每人必须参加，课后现场抽考，过不了加练，考核挂钩下周绩效系数。组长提出销控表更新延迟易引起客诉，总监定为底线问题，要求实时同步、群里喊一声、CRM锁房，再出现直接问责，组长设专人每小时刷新销控大屏。销售A建议邀约话术统一为老业主专属品鉴宴，避开促销字眼；
+销冠建议财务和法务在洽谈区待命，现场签当场出数出收据，成交率能提至少两成，总监协调周六日轮流值班。散会后半小时内组长发会议纪要和任务分解表到工作群。
 # 要点梳理
-## 上月销售数据复盘
-- **总到访**：上月案场总到访320组，环比增加15%，数据达标。
-- **成交与转化**：成交76套，转化率23%，比上月27%下降4个百分点。
-- **来访结构**：渠道带看占比65%，自然来访仅35%。
-- **蓄客与流失**：蓄客量约3200组，认购到成交流失率约18%。
+## 上月数据复盘与转化率问题
+- **到访与成交**：上月案场总到访320组，环比增加15%，达标；成交76套，转化率23%，较上月27%下降4个百分点。
+- **来访结构**：渠道带看占比65%，自然来访仅35%；蓄客量约3200组，认购到成交流失率约18%。
 - **销冠业绩**：销冠上月成交19套，为组内最高。
-- **客户流失抗性**：主要集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、车库层高、外墙保温层）两点。
-- **结论**：整体量够，但卡在逼定和转化环节。
+- **客户流失抗性**：集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、车库层高、外墙保温层）两方面。
+- **总监定性**：量够但转化不足，卡在逼定和转化环节；渠道占比过高反映自主拓客和案场拦截能力退化。
 ## 工地开放日标准化
-- **现状问题**：工地开放日频率不够，客户自行看房不便，陪看占时间；流程繁琐，报备审批需半天。
-- **改进方案**：组长建议每周三下午固定开放，提前在客户群和朋友圈发预告，客户直接对接专属顾问。
-- **决策**：总监要求组长出方案，定在每周三，提前两天在CRM系统推送意向客户。
+- **现状问题**：工地开放日频率不足，客户自行看房不便，陪看占用销售时间；流程繁琐，报备审批需半天。
+- **决策**：定于每周三下午固定开放，提前两天在CRM系统推送意向客户，客户直接对接专属顾问，不走复杂流程。
+- **责任分工**：组长负责出标准化方案。
 ## 价格抗性与逼定策略
-- **算总账方法**：销冠不直接降价，而是拉表对比竞品，说明单价虽高2000元，但十年省下物业和品质维修维护费。
-- **限时权益逼定**：销冠递上“限时权益”逼定函，本周定可申请多送三年物业费，过了这周就没有。
-- **权益具象化**：销售B建议把三年缴费明细打印出来放在合同旁，客户心里有底。
-- **物料问题**：案场逼定函常是上月版本，组长联系设计本周出新版，下月搞“权益可视化”台卡放洽谈区。
+- **政策背景**：下月政策调整，特价房名额有限，可在装修包和车位上做文章。
+- **销冠逼定手法**：不直接降价，算总账对比——单价虽高2000元，但十年省物业费和品质维修维护费；递送“限时权益”逼定函，承诺本周定可申请多送三年物业费。
+- **销售B建议**：将权益具象化，如打印三年缴费明细放在合同旁；现场案场物料更新慢，逼定函常是上月版本。
+- **物料更新**：组长联系设计部门，本周出新版逼定函，把权益条款写清楚；下月制作“权益可视化”台卡放洽谈区。
 ## 跟进节奏与渠道带看质量
-- **跟进提速**：总监强调客户不过夜，人手够，分片包干。
-- **回访安排**：组长带销售A和销售B回访上周未成交的300多组客户，重点盯“再考虑考虑”的。
-- **高意向梳理**：销冠梳理手头20多个高意向客户，看能否周末一波逼定。
-- **渠道实名制**：下月起带看必须实名登记，且有明确需求标签，否则扣减渠道积分。
-- **渠道阻力**：销售A反映中介抵触，怕渠道不愿推项目；总监表示渠道部由他亲自沟通，质量大于数量，底线不能破。
+- **跟进问题**：客户晚上问政策回复慢，热度下降；总监强调“客户不过夜”，分片包干。
+- **回访安排**：组长带销售A和销售B回访上周未成交的300多组客户，重点盯“再考虑考虑”的；销冠梳理手头20多个高意向客户，周末逼定。
+- **渠道带看**：无效带看多，中介随便拉人凑数；下月起带看必须实名登记，有明确需求标签，否则扣减渠道积分。
+- **渠道抵触风险**：销售A担心中介因实名制严格不愿推项目；总监表示亲自与渠道部沟通，质量大于数量，带看质量不行直接换备选。
 ## 老带新政策与业主答谢会
-- **奖励政策**：老带新成功一套奖励两万现金或等值车位券。
-- **当前进展**：销售B本月推4组，2组在谈，客户反馈不错。
+- **奖励政策**：老带新成功一套奖励2万现金或等值车位券；销售B本月推4组，2组在谈。
 - **伴手礼支持**：组长准备定制高端茶叶礼盒和定制保温杯，老业主转介绍时直接送。
-- **业主推荐官活动**：销冠建议每成功推荐一套，升级物业服务等级（优先预约维修、免费家政清洗一次），软性权益更易在小区群传播。
-- **决策**：总监要求组长把方案加进去，下周前出详细执行表。
+- **业主推荐官活动**：销冠建议每成功推荐一套，除现金外升级物业服务等级（优先预约维修、免费家政清洗一次）；组长将方案加入执行表，下周前出详细执行表。
+- **周末答谢会**：销售B计划举办小型业主答谢会，邀请成交业主分享并推老带新政策；销冠协助盯两桌，客群重合度高可联动集中去化。
 ## 下月目标与任务拆分
 - **集团指标**：下月总去化120套，比上月多50%。
-- **拆分方案**：销冠28套；组长+销售A+销售B共50套；机动和渠道攻坚储备12套。
-- **销售A表态**：手头15个准客户等下周认筹通知，只要逼定话术统一、配合资源倾斜，50套能扛下来。
-- **销售B计划**：周末搞小型业主答谢会，邀请成交业主分享，顺便推老带新政策。
-- **联动安排**：销冠协助盯两桌，客群重合度高，把高意向客户先拢到一起，周末集中去化。
+- **任务拆分**：销冠28套；组长+销售A+销售B共50套；剩余12套作为机动和渠道攻坚储备。
+- **销售A表态**：手头有15个准客户，等下周认筹通知；只要逼定话术统一、配合资源倾斜，50套能扛下来。
+- **销售B表态**：通过老带新和自然来访突破，周末答谢会氛围搞好可提升转化率。
 ## 专项培训与销控纪律
-- **专项演练**：本周安排两次——竞品对比与抗性化解、逼定时机与谈判心理学；每人必须参加，课后现场抽考，过不了加练。
+- **培训安排**：本周两次专项演练——“竞品对比与抗性化解”和“逼定时机与谈判心理学”；每人必须参加，课后现场抽考，过不了加练。
 - **考核挂钩**：组长安排签到和考核表，结果直接挂钩下周绩效系数。
-- **销控问题**：销控表更新延迟，客户定了后销售仍推同套房，易引起客诉。
-- **销控纪律**：总监要求销控实时同步，CRM系统同步锁房；再出现丢单或客诉直接问责；组长设置专人每小时刷新销控大屏。
-## 周末答谢会细节补充
-- **邀约话术**：销售A建议统一为“老业主专属品鉴宴”，避开“促销”字眼，客户抵触心理会小很多。
-- **模板修改**：销售B去改邀约短信和电话模板。
-- **财务法务待命**：销冠建议财务和法务在洽谈区待命，现场能签当场出数出收据，成交率能提至少两成。
-- **值班安排**：总监协调财务和法务周六日轮流值班，在案场外围，把服务做前置。
+- **销控问题**：销控表更新延迟，客户定后销售仍推同套房，易引起客诉。
+- **销控纪律**：销控必须实时同步，推房需在群里喊一声，CRM同步锁房；再出现销控不同步丢单或客诉直接问责；组长设置专人每小时刷新销控大屏。
+## 周末答谢会细节与配套
+- **邀约话术**：统一为“老业主专属品鉴宴”，避开“促销”字眼；销售B修改邀约短信和电话模板。
+- **财务法务支持**：逼定时财务和法务在洽谈区待命，现场签当场出数出收据，客户安全感强，成交率能提至少两成；总监协调财务和法务周六日轮流值班，在案场外围。
 ## 结论与决定
-- **工地开放日标准化**：定在每周三，提前两天在CRM系统推送意向客户。
-- **逼定权益可视化**：替换旧版物料，本周出新版，下月搞“权益可视化”台卡。
-- **渠道带看实名制**：必须有明确需求标签，否则扣减渠道积分。
-- **下月目标**：总去化120套，拆分：销冠28套，组长+销售A+销售B共50套，机动12套。
-- **周末业主答谢会**：销冠带人协助，销售B主抓流程，销售A负责客户邀约和逼定记录。
-- **专项演练**：本周两次，每人必须参加，课后现场抽考，过不了加练。
-- **销控纪律**：CRM系统同步锁房，再出现丢单或客诉直接问责。
-- **财务法务值班**：周六日轮流值班，在案场外围。
-- **邀约话术**：统一为“老业主专属品鉴宴”，避开“促销”字眼。
+- **五项核心动作**：工地开放日标准化（每周三固定开放）；逼定权益可视化并更新物料；渠道带看实名制与质量考核；周末业主答谢会联动去化；专项培训与销控纪律。
+- **下月目标**：总去化120套，按销冠28套、组长+销售A+销售B共50套、机动12套拆分执行。
+- **销控底线**：销控实时同步，CRM锁房，再出现丢单或客诉直接问责。
 ## 行动项与分工
-- **组长**：出工地开放日标准化方案，定每周三、提前两天CRM推送；联系设计本周出新版逼定物料；带销售A和销售B回访上周未成交的300多组客户；准备定制伴手礼；下周前出老带新详细执行表；安排专项演练签到和考核表；设置专人每小时刷新销控大屏；散会后半小时内把会议纪要和任务分解表发到工作群。
-- **销冠**：下月目标28套；梳理手头20多个高意向客户，周末逼定；协助周末答谢会盯两桌；下周晨会分享逼定案例。
-- **销售A**：与组长、销售B共扛50套目标；负责周末答谢会客户邀约和逼定记录；手头15个准客户等下周认筹通知。
-- **销售B**：与组长、销售A共扛50套目标；主抓周末答谢会流程；修改邀约短信和电话模板为“老业主专属品鉴宴”。
-- **总监**：与渠道部沟通实名制事宜；协调财务和法务周六日轮流值班；盯渠道和工程对接。
+- **组长**：出工地开放日标准化方案；带销售A和销售B回访上周未成交的300多组客户；准备定制伴手礼；将“业主推荐官”方案加入执行表，下周前出详细执行表；安排培训签到和考核表；设置专人每小时刷新销控大屏；散会后半小时内将会议纪要和任务分解表发到工作群。
+- **销冠**：梳理20多个高意向客户，周末逼定；协助周末答谢会盯两桌；下周晨会分享逼定案例。
+- **销售A**：负责周末答谢会客户邀约和逼定记录；梳理客户池，15个准客户等下周认筹通知。
+- **销售B**：主抓周末答谢会流程；修改邀约短信和电话模板为“老业主专属品鉴宴”；推进老带新（本月已推4组、2组在谈）。
+- **总监**：与渠道部沟通带看实名制；协调财务和法务周六日轮流值班；盯渠道和工程对接。
 ## 待确认与风险
-- **渠道抵触**：中介对带看实名制有抵触，可能不愿推项目，需总监与渠道部沟通。
-- **老带新执行细节**：业主推荐官活动的具体执行细节待组长下周前出方案。
+- **渠道抵触风险**：渠道带看实名制可能引起中介抵触，需与渠道部沟通确认；若带看质量不行，直接换备选。
 - **转化率下降**：从27%降至23%，卡在逼定和转化环节。
 - **渠道依赖**：渠道带看占比65%，自主拓客和案场拦截能力退化。
 - **物料滞后**：逼定函常是上月版本，影响逼定效果。
-- **销控延迟**：客户定了后销售仍推同套房，易引起客诉。</t>
+- **销控客诉风险**：销控表更新延迟，客户定后销售仍推同套房，易引起客诉。</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>75.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4211/5097</t>
+          <t>4211/4298</t>
         </is>
       </c>
     </row>
@@ -17703,76 +17529,71 @@
       <c r="C56" t="inlineStr">
         <is>
           <t># 全文摘要
-本次团队例会由组长主持，A与B两位成员参与，围绕ASR模型迭代、线上推理延迟与长音频卡死问题展开。会议覆盖五个板块：模型训练与数据优化、动态Batching与推理延迟、长音频解码卡死、监控面板与CI评估流水线、前端32k采样率升级。关键结论包括：确认流式RNN-T混合架构与2秒切分方案，本周五前出详细设计和压测数据；加入early stopping机制解决解码卡死，B今晚改完热修复版本、周四提测；监控面板与CI自动评估流水线本周内定稿并对接运维和测试环境；前端32k采样率升级由组长拉会推进。关键数字：有效语音时长占比从89%提升至94%，验证集WER下降0.8个点，首字延迟目标控制在80ms以内、吞吐量稳定在120路并发，组长协调下周一起划拨三块A100用于增量训练。
-会议确认了多项技术方向与分工：模型侧将全纯Transformer架构换成流式RNN-T和Transformer混合形态，先在20小时核心数据上训练，并引入MixUp和Cut增强；推理侧将动态Batching改为静态分段加流式解码，音频按2秒切块、前端VAD预过滤、后端RNN-T增量解码。VAD阈值由B做消融实验，画误切率和漏切率曲线找最优解。长音频卡死问题确认加入early stopping机制（连续30步置信度低于0.2强制截断）和超时熔断降级，组长要求稳定性优先、精度次之，下周出热修复版本上灰度。A负责CI自动评估流水线（周四前出V1版本），B负责监控面板（明天下班前发指标定义文档，告警阈值分P0/P1两级）与前端32k升级对比文档。风险点包括RNN-T的KV Cache显存峰值易飙高、动态Batching首字延迟波动在150ms到300ms、前端采样率不升级会引入高频伪影等。
+本次团队例会由组长主持，A与B两位成员参与，围绕ASR模型迭代、线上推理延迟与长音频卡死三大议题展开。会议覆盖数据与模型训练、推理侧优化、长音频解码稳定性、监控与CI评估流水线、前端采样率升级等板块。关键结论包括：确认流式RNN-T混合架构与2秒切分方案，目标首字延迟控制在80ms以内；针对长音频卡死加入early stopping机制，下周先出热修复版本上灰度，稳定性优先；同时确定CI自动评估流水线与监控面板方案，并协调算力支持。关键数字：有效语音时长占比提升至94%，WER下降0.8个点，显存占用预计降低30%，下周一开始划拨三块A100用于增量训练。
 # 分段速览
-## 00:00:00-00:00:58 开场与数据进展
-组长宣布会议开始，要求A和B分别同步ASR模型迭代、线上推理延迟和长音频卡死问题的进展，有卡点或资源需求当场提出。A汇报数据清洗流水线已完成第二轮，长尾噪音、极端口音和背景人声重叠片段已分流处理，有效语音时长占比从89%提升至94%；同时重新校对了CTC的blank token分布，发现多音字和连读场景的切分点存在偏移，计划用新基准跑消融实验。
-## 00:00:58-00:02:55 模型架构调整讨论
-B反馈验证集WER下降0.8个点，但低资源语言混合边界场景下中英文切换时过渡音易被吞或重复解码。A说明问题源于CTC对齐阶段对跨语言边界和轻声尾音处理不够平滑，计划将全纯Transformer架构换成流式RNN-T和Transformer混合形态，先在20小时核心数据上训练，并引入MixUp和Cut增强。B提醒RNN-T的KV Cache显存峰值易飙高，A回应已评估过，计划对prefix LM缓存做INT8量化配合动态缓存释放策略，可压降约30%显存占用，压测数据明天下午发群。
-## 00:02:55-00:04:35 推理延迟与动态Batching
-B指出动态Batching调度在长短音频混排时首字延迟波动在150ms到300ms，产品反馈体验不连贯，计划改为静态分段加流式解码组合方案：音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，目标首字延迟控制在80ms以内、吞吐量稳定在120路并发。VAD阈值当前卡在-25dB，结合能量和谱熵双模型判断，下周拉线上流量回放做端到端对比。A提醒VAD阈值需平衡误切率和漏切率，要求B拉回放时把前后帧特征打点日志。
-## 00:04:35-00:06:34 组长定调与CI流水线
-组长确认方向可行，提出三点要求：流式架构切换不能影响非流式离线批处理、VAD阈值做消融实验画曲线找最优解、下周划拨三块A100做增量训练但需与NLP组错峰。A回应会分跑离线和流式验证集，周五发测试用例评审，并补充提出用GitLab CI跑自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码和结果对比，WER未下降或RTF超标直接打回，预计三天落地、周四前出V1版本。
-## 00:06:34-00:08:49 长音频卡死与热修复
-B报告线上出现超长连续带方言口音音频导致解码器loop卡死、服务器节点重启的问题，解码器默认max steps为2048个token、超时5秒，但实际序列超长且attention权重震荡未收敛，直接报OOM。A建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，可解决90%以上卡死问题。组长要求稳定性优先、精度次之，下周出热修复版本上灰度，B负责改解码逻辑，A配合长序列数据配比和边界用例验证，B今晚改完、周四提测。
-## 00:08:49-00:10:35 监控面板与采样率升级
-B提出日志系统简陋，线上推理中间特征无法落盘，计划接Prometheus和Grafana监控面板，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标。组长同意并让B出监控指标定义文档，明天下班前发，告警阈值分P0（服务不可用或延迟超500ms）和P1（显存超85%或WER突增）两级。B随后指出前端SDK采样率16k与新模型32k输入不匹配，上采样会引入高频伪影，前端排期推到下月；组长要求拉文档写数据对比和线上收益，明天拉产品和技术总监过一下优先插队。
-## 00:10:35-00:11:57 重采样方案与会议总结
-A担心服务端加重采样模块增加推理链路延迟，建议B先写轻量级重采样插件用libresample实测CPU占用和延迟影响再决策，B回应CPU开销控制在5%以内再提方案。组长总结今日要点：流式RNN-T混合架构和2秒切分方案本周五前出详细设计和压测数据；VAD阈值和长序列解码卡死问题B周四出消融报告和热修复方案；前端32k采样率升级B出对比文档和重采样插件实测；监控面板和CI自动评估流水线本周内定稿并对接运维和测试环境。A周三前发CI脚本和测试用例评审，会议结束。
+## 00:00:00-00:00:19 会议开场
+组长宣布会议开始，明确本次议题为过一遍上周ASR模型迭代进度、线上推理延迟和长音频卡死问题，要求A和B分别同步各自负责板块的现状，有卡点或需协调资源当场提出。
+## 00:00:19-00:02:55 数据与模型训练汇报
+A汇报混合语料库数据清洗流水线已完成第二轮，有效语音时长占比从89%提升至94%，并重新校对了CTC的blank token分布，发现多音字和连读场景切分点有偏差。B反馈验证集WER下降0.8个点，但指出低资源语言混合边界场景存在切分毛刺，中英文切换时过渡音易被吞或重复解码。A回应计划将全纯Transformer架构改为流式RNN-T和Transformer混合形态，先在20小时核心数据上训练，并引入MixUp和Cut增强策略。B对RNN-T缓存机制和显存占用提出疑问，A回应将做INT8量化配合动态缓存释放策略，预计压降30%显存占用，但压测数据未跑完，明天下午发日志和截图。
+## 00:02:55-00:04:50 推理侧延迟优化讨论
+B指出动态Batching调度导致首字延迟波动在150ms到300ms，产品反馈体验不连贯，计划改为静态分段加流式解码组合方案：音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，目标首字延迟控制在80ms以内、吞吐量稳定在120路并发。A提醒VAD阈值需平衡误切率和漏切率，阈值太高会切掉轻声尾音导致缺字，太低则增加无效推理，建议拉线上流量回放时把前后帧特征打点日志。B表示日志模板即改，并询问流式解码与静态切分衔接是否影响热词注入实时生效。
+## 00:04:50-00:06:43 组长三点要求与CI评估流水线
+组长提出三点要求：流式架构切换不能影响非流式离线批处理，测试用例需覆盖全；VAD阈值由B做消融实验画误切率和漏切率曲线找最优解；下周一划拨三块A100给A做增量训练，注意与NLP组错峰。A回应会分跑离线和流式验证集，周五前发测试用例评审，并补充提出用GitLab CI跑自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码、结果对比，WER未下降或RTF超标直接打回。组长认可并要求B的压测脚本也挂上去形成闭环，A预计三天落地、周四前出V1版本，B配合把压测数据输出成标准JSON格式。
+## 00:06:43-00:08:49 长音频卡死问题与热修复方案
+B报告线上出现超长连续带方言口音音频导致解码器loop卡死、服务器节点重启。组长询问解码器max steps和超时熔断配置，B回应默认2048个token、超时5秒，但实际序列超阈值时解码器未优雅降级直接OOM，原因是RNN-T的attention权重震荡未收敛。A建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，能解决90%以上卡死问题。B确认加上该逻辑并做超时熔断和降级返回，组长决定稳定性优先、精度次之，下周先出热修复版本上灰度，B负责改解码逻辑，A配合长序列数据配比和边界用例验证。
+## 00:08:49-00:11:06 监控面板与前端采样率升级
+B提出日志系统简陋、线上推理中间特征无法落盘，计划接Prometheus和Grafana监控面板，可视化QPS、延迟、显存利用率、解码步数、VAD误切率。组长同意并让B出监控指标定义文档明天下班前发，告警阈值分P0和P1两级：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增。B随后指出前端SDK音频采样率仍为16k而新模型是32k输入，上采样会引入高频伪影影响识别率，前端排期推到下个月。组长决定拉文档和产品技术总监优先插队，若前端不升级则服务端加实时重采样模块但会增加CPU开销；A建议B先写轻量级重采样插件用libresample实测CPU占用和延迟影响，B表示CPU开销控制在5%以内再提方案。
+## 00:11:06-00:11:57 会议总结
+组长总结四项要点：流式RNN-T混合架构和2秒切分方案本周五前出详细设计和压测数据；VAD阈值和长序列解码卡死问题B周四出消融报告和热修复方案；前端32k采样率升级由B出对比文档和重采样插件实测、组长拉会推进；监控面板和CI自动评估流水线本周内定稿并开始对接运维和测试环境。A确认周三前发CI脚本和测试用例评审，B确认盯推理优化、VAD消融、热修复和监控文档，会议结束。
 # 要点梳理
-## 数据与模型训练
-- **数据清洗**：混合语料库清洗流水线完成第二轮，长尾噪音、极端口音、背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%
-- **CTC对齐**：重新校对blank token分布，发现多音字和连读场景切分点偏，计划用新基准跑一轮消融
-- **验证集表现**：WER下降0.8个点；低资源语言混合边界场景下，中英文切换时过渡音被吞或重复解码
-- **架构调整**：计划将全纯Transformer换成流式RNN-T和Transformer混合形态，先在20小时核心数据上训练
-- **数据增强**：已加时间偏移，对背景白噪声和混响鲁棒性不足，准备引入MixUp和Cut再迭代
-- **显存优化**：RNN-T的prefix LM缓存做INT8量化，配合动态缓存释放策略，预计压降30%左右显存占用；压测数据未跑完，明天下午发日志和截图
-- **算力协调**：组长协调下周一开始划拨三块A100做增量训练，需与NLP组排队错峰
-## 线上推理延迟与动态Batching
-- **现状问题**：动态Batching在长短音频混排时首字延迟波动在150ms到300ms，产品反馈体验不连贯
-- **优化方案**：改为静态分段加流式解码组合——音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码
-- **性能目标**：首字延迟控制在80ms以内，整体吞吐量稳定在120路并发
-- **VAD阈值**：当前卡在-25dB，结合能量和谱熵双模型判断；组长要求做消融实验，画误切率和漏切率曲线找最优解
-- **线上验证**：下周拉线上流量回放做端到端对比，前后帧特征打点日志便于排查切分点对齐影响
-## 长音频卡死与热修复
-- **故障现象**：超长连续带方言口音音频导致解码器loop卡死，服务器节点重启
-- **根因**：解码器默认max steps为2048个token、超时5秒，实际序列超阈值后未优雅降级直接OOM；RNN-T的attention权重震荡未收敛
-- **修复方案**：加early stopping机制——连续30步置信度低于0.2强制截断并返回当前序列，配合超时熔断和降级返回，预计解决90%以上卡死问题
-- **优先级**：组长明确稳定性优先、精度次之，下周出热修复版本上灰度；专业术语靠后续词表扩展和热词注入解决
-- **数据配比**：A训练时注意长序列数据配比，别全塞短音频
-## 监控与CI评估流水线
-- **CI自动评估**：用GitLab CI跑自动评估流水线，代码合入触发数据拉取、模型加载、测试集解码、结果对比；WER未下降或RTF超标直接打回
-- **落地时间**：A负责写评估脚本和流水线配置，预计三天，周四前出V1版本；B配合把压测数据输出成标准JSON格式
-- **监控面板**：接Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率
-- **告警分级**：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增；监控指标定义文档明天下班前发组长
+## ASR模型迭代与数据优化
+- **数据清洗**：混合语料库数据清洗流水线完成第二轮，长尾噪音、极端口音和背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%
+- **WER表现**：验证集WER下降0.8个点，但低资源语言混合边界场景存在切分毛刺，中英文切换时过渡音易被吞掉或重复解码
+- **架构调整**：A计划将全纯Transformer架构改为流式RNN-T和Transformer混合形态，先在20小时核心数据上训练；数据增强策略加入时间偏移，计划引入MixUp和Cut再迭代一轮
+- **显存优化**：RNN-T的prefix LM缓存计划做INT8量化，配合动态缓存释放策略，预计降低30%显存占用；压测数据和显存曲线未跑完，明天下午发日志和截图
+- **算力协调**：组长协调下周一开始划拨三块A100给A做增量训练，需与NLP组错峰，目前NLP组有四个job在排队，A调整启动脚本优先跑验证集小的实验
+## 线上推理延迟优化
+- **延迟问题**：动态Batching调度导致首字延迟波动在150ms到300ms，产品反馈体验不连贯
+- **方案调整**：B计划改为静态分段加流式解码组合方案，音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，目标首字延迟控制在80ms以内，整体吞吐量稳定在120路并发
+- **VAD阈值**：当前卡在-25dB，结合能量和谱熵双模型判断；A提醒阈值需平衡误切率和漏切率，设太高会切掉轻声尾音导致缺字，设太低增加无效推理
+- **验证计划**：B计划下周拉线上流量回放做端到端对比，前后帧特征打点日志方便排查切分点对齐影响
+- **组长要求**：流式架构切换不能影响非流式离线批处理，双线都要保，测试用例需覆盖全；VAD阈值由B做消融实验，画误切率和漏切率曲线找最优解
+## 长音频卡死问题
+- **问题现象**：线上出现超长连续带方言口音音频，解码器陷入无效循环导致loop卡死，服务器节点重启
+- **根因定位**：解码器默认max steps为2048个token，超时时间5秒；实际解码序列超阈值时未优雅降级直接OOM，RNN-T的attention权重一直震荡未收敛
+- **修复方案**：A建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，预计解决90%以上卡死问题；B负责改解码逻辑并加超时熔断和降级返回
+- **决策口径**：组长决定稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度；A配合长序列数据配比和边界用例验证
+## 监控面板与CI评估流水线
+- **CI流水线**：A计划用GitLab CI跑自动评估流水线，代码合入触发数据拉取、模型加载、测试集解码、结果对比，WER未下降或RTF超标直接打回；预计三天落地，周四前出V1版本
+- **压测对接**：B配合把压测数据输出成标准JSON格式，方便流水线直接读取；组长要求B的压测脚本也挂上去形成闭环
+- **监控面板**：B计划接Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率；监控指标定义文档明天下班前发组长，由组长转发运维负责人
+- **告警分级**：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增
 ## 前端32k采样率升级
-- **问题**：前端SDK音频采样率16k，新模型32k输入，上采样引入高频伪影影响识别率；前端排期推到下个月
-- **收益依据**：32k模型在长尾词上比16k好0.5%的WER
-- **推进方式**：B出数据对比和线上收益文档，组长明天拉产品和技术总监过一下，优先插队
-- **备选方案**：若前端不升级，服务端加实时重采样模块兼容，但增加CPU开销；A建议先用libresample实测CPU占用和延迟影响，B计划CPU开销控制在5%以内再提方案
+- **现状问题**：前端SDK音频采样率16k，新模型为32k输入，上采样会引入高频伪影影响识别率；前端对接人排期推到下个月
+- **推进方式**：组长决定拉对比文档和线上收益说明，明天拉上产品和技术总监过一下优先插队；32k模型在长尾词上比16k好0.5%的WER
+- **备选方案**：若前端不升级，服务端加实时重采样模块兼容但增加CPU开销；A担心推理链路过长增加延迟，建议B先写轻量级重采样插件用libresample实测CPU占用和延迟影响，CPU开销控制在5%以内再提方案
 ## 结论与决定
-- **架构方向**：确认流式RNN-T混合架构和2秒切分方案，A和B分头推进，本周五前出详细设计和压测数据
-- **稳定性优先**：长音频卡死问题先保稳定性、精度次之，加入early stopping机制，下周出热修复版本上灰度
-- **双线保障**：流式架构切换不能影响现有非流式离线批处理，测试用例需覆盖全
-- **监控与CI**：监控面板和CI自动评估流水线本周内定稿，开始对接运维和测试环境
+- **架构确认**：流式RNN-T混合架构和2秒切分方案方向可行，A和B分头推进，本周五前出详细设计和压测数据
+- **修复优先级**：长音频卡死问题先保稳定性，加入early stopping机制和超时熔断降级，热修复版本下周先上灰度
+- **双线并行**：流式架构切换不能影响非流式离线批处理，测试用例需覆盖全
+- **监控与评估**：CI自动评估流水线和监控面板方案确定，本周内定稿并开始对接运维和测试环境
 ## 行动项与分工
-- **A**：周三前把CI脚本和测试用例发群里评审；周四前出评估流水线V1版本；配合长序列数据配比和边界用例验证
-- **B**：今晚改完热修复版本，周四提测；周四出VAD消融报告；明天下班前发监控指标定义文档；出前端32k对比文档和重采样插件实测
-- **组长**：明天拉产品和技术总监过前端32k升级；转发监控指标文档给运维负责人
+- **A**：周三前把CI脚本和测试用例发群里评审；周四前出评估流水线V1版本；本周五前完成流式RNN-T混合架构详细设计和压测数据；配合长序列数据配比和边界用例验证
+- **B**：今晚改完热修复版本，周四提测；周四出VAD阈值消融报告；明天下班前发监控指标定义文档；先写轻量级重采样插件实测CPU占用和延迟影响
+- **组长**：明天拉上产品和技术总监过前端32k采样率升级；协调算力划拨和运维对接
 ## 待确认与风险
-- **显存风险**：RNN-T的KV Cache显存峰值易飙高，INT8量化压测数据未跑完，明天下午发日志和截图确认阈值
-- **VAD阈值**：-25dB在真实线上底噪下是否最优待验证，下周线上流量回放端到端对比确认
-- **前端排期**：32k采样率升级排期未定，需组长拉会推进；服务端重采样模块CPU开销影响未实测
-- **服务稳定性**：长音频解码器loop卡死已导致服务器节点重启，热修复上灰度前需充分验证</t>
+- **显存风险**：RNN-T的KV Cache显存峰值容易飙高，并发量上去可能导致OOM拖垮线上服务；INT8量化压测数据未跑完，明天下午验证
+- **VAD阈值**：-25dB在真实线上环境的底噪下是否合适未验证，需通过线上流量回放确认
+- **架构衔接**：流式解码和静态切分的衔接可能影响热词注入的实时生效
+- **前端升级**：32k采样率升级排期能否提前未定，需组长拉会推进；服务端重采样插件的CPU开销和延迟影响未实测</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>78.7</v>
+        <v>74</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3912/4654</t>
+          <t>3912/4462</t>
         </is>
       </c>
     </row>

--- a/now.xlsx
+++ b/now.xlsx
@@ -567,61 +567,66 @@
       <c r="C2" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲，围绕“走向多极化”主题阐述中国立场。演讲以慕安会报告主题为引，指出世界正走向多极化，中国主张推动平等有序的世界多极化。王毅提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢，并称中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。演讲后，王毅就国际秩序、乌克兰危机、中美关系等议题回应了主持人提问。
+王毅在慕尼黑安全会议上发表演讲，阐述中国对多极化世界的立场。演讲围绕推动平等有序的世界多极化这一主题，提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，中国将坚定做多极体系中的确定性因素，做变革世界中的建设性力量。在随后的问答环节，王毅就国际秩序与规则、乌克兰危机、中美关系等议题回应了主持人提问。
 # 核心信息
-## 核心信息
-- **多极化背景数据**：80年前联合国成立时只有51个会员国，到今天有193个国家；慕安会报告主题为「走向多极化」，中国据此提出推动平等有序的世界多极化。
-- **平等相待主张**：坚持权利平等、机会平等、规则平等，应成为建设多极世界的基本原则；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
-- **国际法治承诺**：中国加入了几乎所有普遍性的政府间国际组织和**600多项国际公约**；从不搞例外主义，更不搞合则用、不合则弃。
-- **联合国会费承担**：中国坚定维护联合国的权威和地位，承担着**超过20%的联合国会费**。
-- **气候履约成果**：中国切实履行`巴黎协定`，建成了**世界上最大的清洁发电体系**。
-- **全球治理倡议**：中国提出并落实`全球发展倡议`、`全球安全倡议`、`全球文明倡议`，为完善全球治理提供公共产品。
-- **经济增长数据**：去年中国GDP增长**5%**，对世界经济增长的贡献率**接近30%**；中国向世界释放超大规模的市场红利。
-- **一带一路对接**：中国愿推动高质量共建`一带一路`，同欧盟的`全球门户`战略相互对接。
-- **中欧关系节点**：今年是中欧建交**50周年**，中方愿同欧方深化战略沟通和互利合作。
-- **国际秩序立场**：中国是在现行国际秩序中发展起来的，是受益者；应共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。
-- **乌克兰危机时间线**：从2022年2月25日（危机爆发第2天）起，中方就提出对话协商解决；习近平主席提出4点主张——各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。
-- **乌克兰问题斡旋行动**：中方派出特使赴各国斡旋，同巴西等南方国家发起`和平之友`；中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识。
-- **中俄关系定位**：中国同俄罗斯建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；中国同俄罗斯之间的交往是正常的国与国之间的交往。
-- **对美政策三原则**：中国对美政策保持连续性和稳定性，即习近平主席提出的相互尊重、和平共处、合作共赢三原则；中方愿意按照三原则同美方构建稳定健康可持续的双边关系。
+## 多极化主张
+- **总体立场**：中国主张推动**平等有序的世界多极化**，这是习近平主席提出的重大主张；中国将坚定做多极体系中的确定性因素、变革世界中的建设性力量。
+- **平等相待**：坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
+- **国际法治**：联合国宪章宗旨和原则是国际关系根本遵循；中国加入几乎所有普遍性政府间国际组织和**600多项国际公约**，从不搞例外主义、不搞合则用不合则弃。
+- **多边主义**：坚持真正的多边主义，倡导共商共建共享的全球治理观；坚定维护联合国权威和地位，承担**超过20%的联合国会费**。
+- **开放共赢**：坚持开放合作，以普惠包容的经济全球化支撑平等有序的世界多极化；去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**。
+## 具体行动与倡议
+- **全球治理公共产品**：提出并落实全球发展倡议、全球安全倡议、全球文明倡议；切实履行巴黎协定，建成世界上最大的清洁发电体系。
+- **共建一带一路**：愿推动高质量共建“一带一路”，与欧盟“全球门户”战略相互对接。
+- **中欧关系**：中方始终认为欧洲是多极世界的重要一极，中欧是伙伴而不是对手；今年是中欧建交50周年，愿用好这一契机深化战略沟通和互利合作。
+## 国际秩序与规则
+- **秩序立场**：中国是在现行国际秩序中发展起来的受益者，要推动秩序朝着更加公正合理的方向发展；真正挑战秩序、毁约退群的是其他国家。
+- **规则共识**：应共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则；反对在遵守国际法上搞双重标准。
+- **台湾问题**：要尊重各国主权和领土完整，就应该支持中国实现完全统一。
 # 官方表态
-**官方表态**（中华人民共和国外交部长 王毅，慕尼黑安全会议演讲）
-## 关于多极化世界
+**官方表态**（中国，王毅，慕尼黑安全会议）
+## 多极化主张
 - **主张**：应当推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是中国对多极世界真诚的期许；中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。
-- **针对**：多极化是否会带来动荡失序、冲突对抗是否意味着大国主导弱肉强食的疑问；列强争霸曾给人类带来灾难，两次世界大战殷鉴不远，不平等的秩序注定土崩瓦解。
-- **条件与前提**：坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则；每一个国家的声音都应该得到倾听，每一个国家都可以在多极格局中找到自身的位置。
+- **针对**：多极化是否会带来动荡失序、冲突对抗是否意味着大国主导弱肉强食的疑问。
 - **承诺**：中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；这不会导致西方的缺失，而将促进世界的正和。
-## 关于国际法治
+- **边界**：中国从不搞例外主义，更不搞合则用、不合则弃。
+## 国际法治
 - **主张**：应当尊重国际法治，联合国宪章宗旨和原则是处理国际关系的根本遵循，也是建设多极世界的重要基石；多极格局不能是无序的状态。
-- **针对**：当今世界乱象频出，一个重要原因就是有些国家迷信实力至上，打开了丛林法则的潘多拉盒子；大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈。
-- **承诺与边界**：中国坚定维护国际法治权威，积极履行国际责任和义务，加入了几乎所有普遍性的政府间国际组织和600多项国际公约；从不搞例外主义，更不搞合则用、不合则弃。
-- **条件**：在遵守国际法上不能搞双重标准；要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
-## 关于多边主义
-- **主张**：应当践行多边主义，联合国是践行多边主义、推进全球治理的核心平台，已经为各国遮风挡雨80年；未来的多极世界更加需要联合国，对于这座大厦应该固本强基，而不是拆梁毁柱。
-- **针对**：面对层出不穷的全球性挑战，没有哪一个国家能够独善其身，搞本国优先只会造成各方的多输；对于治理全球难题应当共担责任，而不是唯利是图；对于共同挑战应该团结应对，而不是阵营对抗。
-- **承诺**：中国坚持真正的多边主义，倡导共商共建共享的全球治理观；坚定维护联合国的权威和地位，承担着超过20%的联合国会费；切实履行巴黎协定，建成了世界上最大的清洁发电体系；提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
-## 关于开放共赢
-- **主张**：应当坚持开放合作，以普惠包容的经济全球化来支撑平等有序的世界多极化；发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。
-- **针对**：保护主义不是出路，滥加关税没有赢家；脱钩断链断的是机遇，小院高墙封的是自己。
-- **承诺**：中国坚定同各国共享发展机遇，去年中国GDP增长5%，对世界经济增长的贡献率接近30%，担当起全球经济增长的重要引擎，向世界释放超大规模的市场红利；愿推动高质量共建“一带一路”，同欧盟的“全球门户”战略相互对接，赋能彼此也赋能世界。
-## 关于中欧关系
-- **主张**：中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手。
-- **承诺**：今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作，推动世界走向和平、安全、繁荣、进步的光明前景。
+- **针对**：当今世界乱象频出，有些国家迷信实力至上，打开了丛林法则的潘多拉盒子。
+- **要求**：大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈；在遵守国际法上不能搞双重标准。
+- **承诺**：中国坚定维护国际法治权威，积极履行国际责任和义务，加入了几乎所有普遍性的政府间国际组织和600多项国际公约。
+- **条件**：要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
+## 多边主义
+- **主张**：应当践行多边主义，联合国是践行多边主义、推进全球治理的核心平台；对于这座大厦应该固本强基，而不是拆梁毁柱。
+- **针对**：面对层出不穷的全球性挑战，搞本国优先只会造成各方的多输。
+- **承诺**：中国坚持真正的多边主义，倡导共商共建共享的全球治理观，坚定维护联合国的权威和地位，承担着超过20%的联合国会费；切实履行巴黎协定，建成了世界上最大的清洁发电体系；提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
+## 开放共赢
+- **主张**：应当坚持开放合作，以普惠包容的经济全球化来支撑平等有序的世界多极化；保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己。
+- **承诺**：中国坚定同各国共享发展机遇，愿推动高质量共建"一带一路"，同欧盟"全球门户"战略相互对接，赋能彼此也赋能世界。
+- **针对**：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。
+- **定位**：中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手；今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作。
+## 国际秩序与规则
+- **主张**：中国是在现行国际秩序中发展起来的，是受益者；要推动这个秩序朝着更加公正合理的方向发展。
+- **针对**：有人说中国要改变秩序、要另起炉灶；真正要挑战秩序、毁约退群的国家已经出现。
+- **要求**：需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数；只要认同这一点，双重标准就不会出现。
+## 人类命运共同体
+- **主张**：习近平主席提出各国共同构建人类命运共同体的重大理念，希望各国超越历史文化社会制度意识形态的不同，以同舟共济的精神共同呵护人类唯一可以居住的星球。
+- **承诺**：中国将继续为践行这些重要理念做出努力和贡献；这体现了中国共产党的国际主义情怀和天下为公的中华优秀文化传统。
 # Q&amp;A环节
-**1. 主持人**：您提到国际秩序，我注意到各方对联合国宪章存在质疑——俄罗斯入侵乌克兰、美国总统威胁使用武力入侵格陵兰和巴拿马、巴勒斯坦人流离失所，贵国也被指控违反海洋法和《世界人权宣言》。您即将前往纽约参加安理会会议，您是否仍相信联合国和联合国宪章？宪章改革在您的优先事项中占多大比重？
-**王毅**：你的提问涉及秩序和规则两个关键词。关于秩序，这几年有人说中国要改变秩序、另起炉灶，但现在说这种话的人可能不多了——真正挑战秩序、毁约退群的国家已经出现，欧洲的朋友可能每天都在感受到阵阵寒意。中国是在现行国际秩序中发展起来的，是受益者，我们要做的是按照大多数国家的愿望推动秩序朝着更加公正合理的方向发展。关于规则，我们起码应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。只要认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字、治理赤字，共同构建人类命运共同体。
-**2. 主持人**：2022年慕安会前几天您曾表示任何国家的主权、独立和领土完整都应得到尊重和维护，乌克兰也不例外。如今俄罗斯已成为中国有军队的加油站，您对乌克兰有巨大影响力。在要求结束战争的压力增大之际，您能否采取措施——比如减少从俄罗斯购买天然气、降低价格或停止输送两用物资——以加大对俄施压？
-**王毅**：中国同俄罗斯是两大邻国，有着漫长边界，两国关系经历过曲折后吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。关于不从俄罗斯买油气的问题——如果中国不从俄罗斯买，哪个国家能提供如此巨量的油气满足中国民众需求？那是不可能的，也是不保险的，因为有的国家常把经贸问题政治化、当作打压中国的工具，我们不会允许这种情况，要为人民负责任。中国在地区热点问题上有自己的立场：历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出四点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。我们以此推进劝和促谈，派特使斡旋，同巴西等南方国家发起和平之友。任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括美俄达成的共识；所有当事方和利益攸关方应适时参与和谈，欧洲更有必要发挥作用，共同探讨欧洲长治久安，找到均衡、有效、可持续的欧洲安全框架。
-**3. 主持人**：时间所剩不多，能否简要预告您对中美关系将如何发展的看法？
-**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不同是各自人民的选择，想改造或颠覆对方不切实际，正确态度是相互尊重，这是中美交往的前提；和平共处理所当然，两个大国总不能冲突起来，那将殃及整个世界，所以要开展对话、加强交往、增进了解、建立信任；合作共赢是因为国际社会期待中美合作，全球性挑战需要中美携手应对，也是两个大国应承担的国际责任。中方已准备好按三原则同美方构建稳定健康可持续的双边关系，希望美方相向而行；如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼，新中国就是在战胜各种艰难险阻中发展壮大起来的。我们对世界前途和中美关系未来都充满信心，中美共同努力的方向就是相互尊重、和平共处、合作共赢。</t>
+**1. 主持人**：您提到国际秩序，现在很多国家质疑联合国宪章。俄罗斯入侵乌克兰，美国总统威胁使用武力入侵格陵兰和巴拿马、驱逐巴勒斯坦人，中国也被指责违反海洋法和《世界人权宣言》。您即将前往纽约参加安理会会议，您还相信联合国和联合国宪章吗？是否致力于推动联合国改革？
+**王毅**：我不愿意回答周琦先生的提问。关于秩序，这几年总有人说中国要改变秩序、另起炉灶，但现在说这种话的人可能不多了，因为真正挑战秩序、毁约退群的国家出现了。中国是在现行国际秩序中发展起来的，是受益者，我们要做的是按照大多数国家的愿望推动秩序朝更加公正合理的方向发展。关于规则，我们起码应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。只要大家认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字、治理赤字，共同构建人类命运共同体。
+**2. 主持人**：2022年慕安会前几天您曾说任何国家的主权、独立和领土完整都应得到尊重和维护，乌克兰也不例外。如今俄罗斯已成为中国有军队的加油站，您对乌克兰有很大影响力。现在压力加大，您能否采取措施，比如减少从俄罗斯购买天然气、降低价格或停止输送军民两用物资，以施压俄罗斯结束战争？
+**王毅**：中国同俄罗斯是两大邻国，有着漫长边界，两国关系经历过曲折后吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。如果中国不从俄罗斯买油气，哪个国家能提供如此巨量的油气满足中国民众需求？那是不可能的，也是不保险的，因为有的国家常把经贸问题政治化，当作打压中国的工具。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。我们派特使斡旋，同巴西等南方国家发起和平之友。中方乐见一切和平努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应适时参与和谈进程。这场战事发生在欧洲大地上，欧洲更有必要发挥重要作用，共同探讨欧洲长治久安，找到均衡有效可持续的欧洲安全框架。
+**3. 主持人**：时间有限，能否简要预告您认为美中关系将如何发展？
+**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不一样，是各自人民做出的选择，想改造或颠覆对方不切实际。相互尊重是中美交往的前提，和平共处理所当然，中美两个大国总不能冲突起来，那将殃及整个世界。中方已准备好按照三原则同美方构建稳定健康可持续的双边关系。我们希望美方相向而行，但如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼，对世界前途和中美关系的未来都充满信心。中美两国只有一个共同努力的方向，就是相互尊重、和平共处、合作共赢。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>41.7</v>
+        <v>45.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/4142</t>
+          <t>7004/3762</t>
         </is>
       </c>
     </row>
@@ -788,86 +793,80 @@
       <c r="C3" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-本次沟通为电子科技大学电子科学与工程学院面向考生及家长的招生宣讲直播，由学院段院、柳教授、张教授、李天明教授及在读博士田雨桐作为分享嘉宾，主持人负责串场与互动。沟通旨在向考生和家长系统介绍学院整体情况、各学科方向（电子信息材料与元器件、电磁场与微波技术、电路与系统、物理电子学）及人才培养成果，以吸引优秀生源报考。整体基调为积极推介：学院展示了历史沿革、师资科研实力、国家级平台及学生发展出口，田雨桐博士从学生视角补充了择校理由与建议；直播尾声回应了考生关心的夏令营问题，明确学院计划今年举办但时间待定，并公布了咨询QQ群，整体沟通顺畅、信息充分。
+本次宣讲会由电子科技大学电子科学与工程学院主办，面向考生和家长介绍学院整体情况、学科方向、师资科研与人才培养，并解答夏令营等问题。学院源于1956年建校时的无线电系，历经4次院系调整，2023年成立电子科学与工程学院与基层电路学院；电子科学与技术为国家重点一级学科，下设5个二级学科方向，另有3个国防特色学科。本科生1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业）和电磁场与无线技术（国家级一流本科专业建设点）；研究生1975人。现有教师302人，其中两院院士2人、领军人才19人、青年人才28人；近5年科研经费到账稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利授权1300余件。电子信息材料与元器件方向由柳教授介绍，以材料为基础、器件为核心、应用为目标导向，涉及电子材料与电子器件的设计、研制、生产与应用。2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍，先进电子材料元器件电路系统等为卡脖子问题之一。研究团队包括邓龙江院士的电磁辐射控制材料与技术团队（19人，正高13人、副高15人）和张怀武教授的磁电薄膜与微型器件团队（17人，正高15人、副高2人），依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室两个国家级平台。科研面积2万余平米，大型设备500余台套；获国家科技奖项共7项，毕业生去向包括英特尔、中芯国际、华为、德州仪器等。电磁场与微波技术、电路与系统方向由张教授介绍。电磁场与微波技术包含4个细分方向，电路与系统包含3个方向；电磁场与微波技术学科始于1956年，由林卫干先生和谢楚芳先生创建，所属一级学科入选双一流A类。硬件平台拥有中国高校最先进的微波暗室群体和微波毫米波太Hz仿真测试平台。杨世文教授团队的四维天线阵列技术应用于中电14所某大型机载相控阵雷达；樊勇教授团队研制出0.22THz、0.34THz、0.42THz雷达成像系统，分辨率小于1厘米，成果在2023年成都大运会田径项目示范应用。电路与系统学科1981年开始招收研究生，1988年成立首批博士后流动站，拥有国家级人才4人、教授10人、副教授22人。物理电子学方向由李天明教授介绍，是物理学与电子科学与技术的交叉学科，典型应用包括微波电子学、光电子学等。学校物理电子学起源于1956年建校时的电子控器件专业，1979年成立高能电子学研究所，2018年并入电子科学与工程学院。纵向发展包括上游仿真设计（如自主知识产权商用软件MMST和切皮克）和下游系统应用（如毫米波雷达、无线输能系统、微波能干燥系统）；横向发展包括频段上移至毫米波、太赫兹，以及与医学交叉的太赫兹成像诊断。每年到校科研经费接近2亿元，为学院最多；团队学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他。学生代表田雨桐（2023级电子科学与技术专业博士研究生）从学生视角分享选择电子学院的8个理由，包括城市（成都为四川省会、国家中心城市、新一线城市，电子信息产业发达）、学校（电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一）、专业、团队（学院拥有四大学科和19个科研团队）、奖助体系等。田雨桐所在毫米波技术与系统应用团队负责人为樊勇老师，研究方向覆盖微波毫米波理论与技术、天线理论与技术等五大方向；团队硕博毕业生就业率100%，就业单位包括民营企业、大型央国企和头部科研院所。建议先选研究团队再选导师，可通过学院网站、文献检索网站（如IEEE、中国知网）了解导师情况。互动环节中，主持人询问夏令营时间形式，段院回应电子学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群发布；咨询QQ群号确定为978499108。抽奖口令为“E生一世，逐梦未来”。
 # 核心信息与数据
 ## 学院概况
-- **历史沿革**：1956年建校之初成立无线电系、电真空器件系、无线电零件系，经1979年、1992年、2001年、2018年4次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与基层电路学院。
-- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。
+- **历史沿革**：1956年建校时成立无线电系、电真空器件系、无线电零件系，历经1979年、1992年、2001年、2018年4次院系调整成立电子科学与工程学院（示范性微电子学院），2023年响应国家号召成立电子科学与工程学院与集成电路学院。
+- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向；另有电磁场与微波军用关键材料、电子元器件等3个国防特色学科。
 - **党建荣誉**：学院党委入选教育部首批全国党建工作标杆院系，学院荣获全国教育系统先进集体。
-- **人才培养规模**：本科生现有1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向；研究生现有硕士和博士1975人。
-- **研究生招生专业**：学术型博士和硕士为电子科学与技术、材料科学与工程；专业学位博士和硕士为电子信息、材料工程。
+- **人才培养规模**：本科生现有1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业）和电磁场与无线技术（国家级一流本科专业建设点）两个专业方向；研究生现有硕士和博士1975人，招生专业包括电子科学与技术、材料科学与工程等。
 - **师资队伍**：现有教师302人，其中教研系139人、科研系95人、教学系14人、实验系21人、机关33人；两院院士2人、领军人才19人、青年人才28人、其他类型人才12人。
-- **科研经费与成果**：近5年科研经费到账稳定在3-4亿元，以纵向项目为主；牵头获国家科技奖励11项，发表高水平学术论文2000余篇，专利申请1600余件、授权1300余件。
-- **科研团队**：共20个科研团队，年度经费过千万元的团队15个，其中过亿元团队1个。
-- **科研平台**：拥有国家电子辐射控制材料工程技术研究中心、微波电子工器件国家级重点实验室两个国家级平台，4个国际合作平台，7个省部级科研平台；共建国际姊妹院系两个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
+- **科研经费与成果**：近5年科研经费到账稳定在3—4亿元之间，项目以纵向为主、横向为辅；牵头获国家科技奖励11项，发表高水平学术论文2000余篇，专利申请1600余件、授权1300余件。
+- **科研团队与平台**：共有20个科研团队，年度经费过千万元的团队15个、过亿元团队1个；拥有国家电磁辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室两个国家级平台，4个国际合作平台、7个省部级科研平台。
+- **国际交流**：共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
 ## 电子信息材料与元器件方向
-- **方向内涵**：以电子在物质中的输运特性（电磁声光热力、化学生物等）为基础，设计研究和生产电子器件，以材料为基础、器件为核心、应用为目标导向。
-- **产业背景**：2021年中国集成电路电子产品进口额度达2.8万亿元，约为原油进口量的1.7倍；先进电子材料元器件电路系统等电子产品是我国目前最为紧迫的卡脖子问题之一。
-- **应用领域**：电子产品广泛应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子、物联网、移动设备、无人驾驶、航空航天、医疗健康和可穿戴设备等领域，达到万亿美元量级。
-- **发展趋势**：电子产品向小型化、多功能、低功耗、智能化发展，元器件朝微型化、片式化、集成化、薄膜化和智能化方向，材料和器件一体化，摩尔定律与超摩尔定律两条路线结合。
-- **邓龙江院士团队**：电磁辐射控制材料与技术团队，现有研究人员19人（正高13人、副高15人），近年发表包括Nature在内的论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步或技术发明二等奖共计3项。
-- **张怀武教授团队**：磁电薄膜与微型器件团队，现有研究人员17人（正高15人、副高2人），开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目等100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
-- **国家电磁辐射控制材料工程技术研究中心**：历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级形成国家级平台，开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地。
-- **电磁薄膜与集成器件全国重点实验室**：2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建，围绕电子薄膜材料和集成器件开展研究，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向。
+- **方向内涵**：以电子在物质中的输运特性（电磁声光热力、化学生物等）为基础，涉及电子材料、器件、电路的设计研制生产与应用，以材料为基础、器件为核心、应用为目标导向。
+- **产业背景**：2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍；先进电子材料元器件电路系统等为当前最紧迫的卡脖子问题之一。
+- **应用领域**：电子产品在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域起重要作用，已广泛应用于物联网、移动设备、网络基础设施、无人驾驶、航空航天、医疗健康和可穿戴设备，市场规模达万亿美元量级。
+- **发展趋势**：电子产品向小型化、多功能、低功耗、智能化发展，元器件朝微型化、片式化、集成化、薄膜化、智能化方向演进，强调材料和器件一体化；集成技术结合摩尔定律制程缩小与超摩尔定律功能多样化两条路径。
+- **邓龙江院士团队**：电磁辐射控制材料与技术团队，现有研究人员19人（正高13人、副高15人），近年发表包括Nature在内的论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步奖或技术发明奖二等奖共计3项。
+- **张怀武教授团队**：磁电薄膜与微型器件团队，现有研究人员17人（正高15人、副高2人），重点开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目等100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
+- **国家电磁辐射控制材料工程技术研究中心**：历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级形成国家级平台，主要开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地。
+- **电磁薄膜与集成器件全国重点实验室**：2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建，围绕电子薄膜材料和集成器件开展基础应用与工程应用研究，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向。
 - **研究条件**：科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备或系统500余台套；薄膜材料制备设备50余台套，微纳加工设备30台套（含步进式光刻机、反应离子刻蚀机等），微观表征设备10余台套，材料性能测试设备50余台套。
-- **毕业生去向**：遍布产业界与学术界，包括英特尔、中芯国际、华为、德州仪器及高校科研院所。
-- **学生成果**：在读学生杨伟豪以第一作者在自然电子、自然通讯各发表一篇学术论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；毕业生黄飞获斯坦福大学攻读博士全额奖学金；李凤霞读博期间发表学术论文16篇（一作6篇）；严巍获21届王大珩光学奖，以优秀青年学者身份加入苏州大学；毕业生万位任河北美泰电子科技公司副总，采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
-## 电磁场与微波技术与电路与系统方向
+- **毕业生去向**：遍布产业界与学术界，包括英特尔、中芯国际、华为、德州仪器及高校科研院所；在读学生杨伟豪以第一作者在Nature Electronics、Nature Communications各发表论文1篇，5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖。
+## 电磁场与微波技术、电路与系统方向
 - **专业构成**：电磁场与微波技术包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
-- **学科历史**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类学科。
-- **科研团队**：电磁场与微波技术学科由6个团队组成：电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
-- **学科平台**：包含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室；硬件方面拥有中国高校最为先进的微波暗室群体及微波毫米波太赫兹仿真测试平台。
-- **天线方向成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能；在强耦合超宽带相控阵方面取得进展，应用成果应用于中电14所某大型机载相控阵雷达。
-- **毫米波与测量成果**：樊勇教授团队研究毫米波平面集成天线，可应用于毫米波通信雷达系统；李恩教授团队引领微波毫米波测量技术，突破众多技术封锁，有60多年技术积累；杨世文教授团队电磁测井仪器获国家科技进步二等奖一项，成果在中海油推广应用。
-- **微波毫米波电路成果**：延波教授团队引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委支持，应用于新一代高速通信系统；在固态合成功率源、天线阵列、扩电网络等电路与通信雷达系统取得成果；研制出三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端。
-- **计算电磁学与太赫兹成果**：杨世文教授团队计算电磁学相关算法被评为20世纪十大算法之一；樊勇教授团队成功研制0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米，太赫兹通信成果在2023年成都大运会田径项目成功示范应用。
-- **电磁波应用成果**：李恩教授团队在电磁波与物质互作用机理及测评系统方面面向5G通信、高性能系统、生物医学、新能源等方向提供应用需求；在生物医学电磁学及成像方向发表大量高水平论文，有20余项国家发明专利。
-- **电路与系统学科沿革**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站，包含教育部国际合作联合实验室及国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
-- **电路与系统研究成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制；樊勇教授和张静（本人）团队从事毫米波通信雷达CMOS芯片研究；康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统和雷达系统成果。
-- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖，学生获互联网+奖项及各类国际奖项；就业领域包括华为、中兴等行业领军企业、各大研究所和高校。
+- **学科历史**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类。
+- **科研团队**：电磁场与微波技术方向由6个团队组成，包括电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
+- **硬件平台**：拥有中国高校最先进的微波暗室群体，以及先进的微波毫米波太赫兹仿真测试平台。
+- **天线与电磁兼容成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能；强耦合超宽带相控阵成果应用于中电14所某大型机载相控阵雷达；电磁测井仪器获国家科技进步二等奖1项，成果在中海油推广应用。
+- **微波毫米波电路成果**：延波教授团队引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委支持，应用于新一代高速通信系统；研制出三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端等微系统成果。
+- **太赫兹成果**：樊勇教授团队研制出0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米；太赫兹通信成果在2023年成都大运会田径项目成功示范应用。
+- **计算电磁学成果**：杨世文教授团队引领的计算电磁学相关算法被评为20世纪十大算法之一。
+- **电路与系统学科概况**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站；拥有教育部国际合作联合实验室、国家高等学校学科创新引智基地，国家级人才4人、新世纪人才2人、教授10人、副教授22人。
+- **电路与系统研究成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制；樊勇教授和张静直（本人）团队研究毫米波通信雷达CMOS芯片；康凯教授团队在毫米波CMOS芯片方向研制超宽带模块级芯片及5G通信和雷达系统。
+- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖；学生获互联网+奖项、国际HPV奖项等；就业领域包括华为、中兴等行业领军企业、各大研究所和高校。
 ## 物理电子学方向
-- **学科定义**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学中产生新电子器件，典型包括微波电子学（微波电真空器件）和光电子学（光电器件）。
-- **学科特点**：内容不断充实（量子电子学内容逐渐增加），学科边界不一定清晰（光电子学也可属于光学工程一级学科）；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
-- **学校发展历程**：起源于1956年建校时在前苏联专家帮助下成立的电子控器件专业，归属电子器件系；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年并入现在的电子科学与工程学院。
-- **纵向发展**：上游发展仿真设计、数字模拟材料，拥有自主知识产权的商用软件MMST和切皮克（国内广泛应用的两款算法），并将人工智能引入器件设计和电子学应用；下游发展系统应用，研制了毫米波雷达（回旋行波管）、无线输能系统（行波管）、微波能干燥系统（磁控管）。
-- **横向发展**：频段从微波上移至毫米波到太赫兹；与医学交叉，利用太赫兹成像提高医学诊断准确性，利用太赫兹宽频带特点做保密通信和高速通信。
-- **科研经费与平台**：每年到校科研经费接近2亿元，为学院最多；拥有3个四川省工程中心或重点实验室；2023年成功举办行业顶级会议；是国际上最大的真空器件研究中心。
-- **科研团队**：物理电子学方向共有9个团队。
-- **学生出口**：团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；李天明教授个人每年基本两个研究生毕业、一个博士毕业。
+- **学科定义**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学产生新电子器件；典型应用包括微波与电子相互作用形成的微波电子学（微波电真空器件）、光与电子相互作用形成的光电子学（光电器件）。
+- **学科特点**：内容不断充实（如量子电子学内容逐渐增加），学科边界不一定清晰（如光电子学也可属于光学工程一级学科）；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
+- **学校发展历程**：起源于1956年建校时在前苏联专家帮助下成立的电子控器件专业（归属电子器件系）；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年物理电子学院、电工学院和微工学院部分合并成立现在的电子科学与工程学院。
+- **纵向发展**：上游为仿真设计（拥有自主知识产权商用软件MMST和切皮克，并引入人工智能方向），下游为系统应用（用回旋行波管研制毫米波雷达、用行波管做无线输能系统、用磁控管做微波能干燥系统）。
+- **横向发展**：频段从微波上移至毫米波、太赫兹；与医学交叉，利用太赫兹成像提高医学诊断准确性；利用太赫兹宽频带特点做保密通信和高速通信。
+- **科研经费与地位**：每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心；2023年成功举办行业顶级会议；拥有3个四川省工程中心或重点实验室。
+- **团队与学生出口**：物理电子学方向共有9个团队；团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）。
 ## 学生视角分享
-- **城市优势**：成都是四川省会、国家中心城市、新一线城市、国家历史文化名城，电子信息产业发达，从英特尔、华为到京东方等众多行业巨头汇聚，提供实践平台和就业资源。
-- **学校优势**：电子科技大学是我国电子信息人才培育的代名词，拥有电子信息博物馆（记录我国第一台晶体管收音机的诞生），构建了最完整的电子信息学科群。
+- **城市优势**：成都为四川省会、国家中心城市、新一线城市、国家历史文化名城，电子信息产业发达，从英特尔、华为到京东方等巨头汇聚，提供实践平台和就业资源。
+- **学校优势**：电子科技大学是我国电子信息人才培育的代名词，拥有电子信息博物馆（记录我国第一台晶体管收音机诞生），构建了从电子科学与技术、信息与通信工程到集成电路科学与技术的最完整电子信息学科群。
 - **学科实力**：电子科学与技术学科在第4轮学科评估中斩获A+，稳居全国第一；学院拥有四大学科和19个科研团队。
-- **团队选择**：田雨桐所在毫米波技术与系统应用团队，负责人为樊勇老师，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，覆盖电磁场与微波技术、电路与系统，可学到从芯片、封装、天线、电路、模块到系统的全面知识。
-- **就业情况**：团队硕博毕业生实现100%就业率，就业单位有各类民营企业、大型央国企和头部科研院所。
-- **校园印象**：2021年跨年学校在主楼前用300架无人机拼出电子科大英文简称UESTC字样。
-- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金及校园地国家助学贷款和生源地助学贷款。
-- **择校建议**：根据研究方向先选择研究团队再选择导师，可从学院网站按兴趣选择团队，借助文献检索网站（如IEEE、中国知网）检索导师论文情况和指导研究生毕业情况，提前沟通交流。
+- **团队情况**：田雨桐所在毫米波技术与系统应用团队负责人为樊勇老师，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，覆盖从芯片、封装、天线、电路、模块到系统的全面知识。
+- **就业情况**：团队硕博毕业生实现100%就业率，就业单位包括各类民营企业、大型央国企和头部科研院所。
+- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金，以及校园地国家助学贷款和生源地助学贷款。
+- **择校建议**：先根据研究方向选择研究团队，再选择导师；可通过学院网站和文献检索网站（如IEEE、中国知网）检索导师论文情况和指导研究生毕业情况，结合兴趣广泛调研。
 # 各方立场与诉求
-- **主持人**：提出考生和家长关心的夏令营问题，询问电子学院夏令营是否有具体时间和形式。
-- **段院**：回应称电子学院计划今年举办夏令营活动，但具体时间待定，建议感兴趣的同学加入QQ群，相关信息将及时发布。
-- **主持人**：补充说明同学们可扫码或通过群号加入咨询QQ群，并念出群号978499108供考生和家长添加咨询。
-- **考生及家长**：通过弹幕区提出夏令营相关问题，主持人汇总后向段院转达；直播结束前参与抽奖互动，口令为「一生一世，逐梦未来」，奖品为学校马克杯套装。
+- **主持人**：关注夏令营的具体时间与形式，向段院提出咨询。
+- **段院**：回应称电子学院计划今年举办夏令营活动，但具体时间待定，建议考生和家长加入咨询QQ群（978499108），相关信息将及时在群内发布。
+- **主持人**：补充说明考生和家长可扫码或通过群号加入QQ群进行详细咨询和了解。
+- **主持人**：在直播尾声组织抽奖互动，邀请段院及三位老师共同公布抽奖口令“E生一世，逐梦未来”，并宣布中奖同学可通过私信后台留下联系方式和收货地址领取奖品。
 # 达成共识
-- **夏令营安排**：电子学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群发布。
-- **咨询渠道**：咨询QQ群号确定为978499108，考生和家长可扫码或搜索群号加入，获取后续通知。
-- **直播互动**：本场直播抽奖口令为“一生一世，逐梦未来”，奖品为学校马克杯套装，中奖观众需私信后台留下联系方式和收货地址。
+- **夏令营安排**：电子学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群及时发布。
+- **咨询渠道**：学院咨询QQ群号确定为**978499108**，考生和家长可扫码或搜索群号加入，进行详细咨询和了解。
+- **抽奖口令**：本场直播抽奖口令为“E生一世，逐梦未来”，中奖同学需私信后台留下联系方式和收货地址，奖品为学校定制马克杯一套。
 # 待协调事项与后续
 ## 待协调事项
-- **夏令营活动**：电子学院计划今年举办，具体时间与形式待定，相关信息将通过QQ群发布
+- **夏令营活动**：电子学院计划今年举办，具体时间与形式待定，相关信息将通过QQ群及时发布
 ## 后续安排与参与方式
-- **咨询QQ群**：978499108，考生和家长可扫码或搜索群号加入，获取夏令营及学院招生相关信息
-- **抽奖奖品**：电子科技大学马克杯套装（含勺子和杯盖，印有学校logo），中奖同学可私信后台留下联系方式和收货地址，奖品将派送到家
-- **直播互动**：抽奖口令为“一生一世，逐梦未来”，中奖名单包括“小提琴同学”“小镇里的人”“4830同学”“魏军老同学”等
-- **后续沟通**：主持人表示期待在夏令营或研究生入学时与考生和家长面对面沟通交流</t>
+- **咨询QQ群**：978499108，考生和家长可扫码或搜索群号加入，进行详细咨询与了解
+- **抽奖活动**：口令为「E生一世，逐梦未来」，中奖同学可私信后台留下联系方式和收货地址，奖品为电子科技大学整套马克杯（含勺子和杯盖，印有学校logo）
+- **后续沟通**：学院期待在夏令营或研究生入学时与考生和家长进行面对面沟通交流</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>86.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/5799</t>
+          <t>13887/6643</t>
         </is>
       </c>
     </row>
@@ -1404,152 +1403,134 @@
       <c r="C4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次复盘会为公司2023年度总结暨年终奖颁发年会，由老板主持，围绕年度经营数据、年终奖发放标准、员工评价与颁奖、各部门总结及抽奖福利展开。预期目标为总结2023年发展状况、公布年终奖并展望2024年。实际结果方面，年终奖总额为226,000元，成本支出390万元，利润率约24%或27%；最高工资（含年终奖）有2-3人达20万元以上，平均到手工资1万多元。老板指出成本控制是最大问题，根源在于老板管理不足；公司总量提升、员工收入提升，但成本上升导致结余缩水，老板个人收入比去年少约10万，并承担了亏损100万的风险。会上逐一评价员工并颁发最佳新人、最佳进步、后期独挡一面、最佳员工、特别贡献五个奖项，各部门总结显示短视频账号粉丝大幅增长但变现项目未完成，执行部门项目未做砸，商务部门实打实项目约300万左右。
+本次复盘会为2023年度总结暨年终奖颁发会议，由老板主持，围绕年度经营数据、年终奖发放标准、员工评价与颁奖、部门总结及抽奖福利等环节展开。预期目标为总结2023年公司发展状况、公布年终奖并展望2024年。实际结果方面，老板公布年终奖总额226,000元，成本支出（人员工资、外援配音、字幕、租机器）390万元，利润率约24%或27%；最高工资（含年终奖）有2-3人达到20万元以上，平均到手工资1万多元。老板指出成本控制是最大问题，根源在于老板管理不足；公司总量提升、员工收入提升，但成本上升导致结余缩水，老板个人收入比去年少约10万。会议逐一评价员工并颁发最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（市井）、最佳员工奖（游腾宇）、特别贡献奖（李海腾）等五项奖项；各部门总结显示短视频账号粉丝大幅增长但变现重点项目未完成，后期部门加班严重，商务部门实打实项目约300万。
 # 结果与关键成果
 ## 交付与里程碑
-- **账号运营**：郭东辉负责的短视频账号在2023年实现多平台粉丝大幅增长，视频号从3月1日的719人涨至8万，小红书从2000+涨至6.4万，抖音从2000+涨至5.7万，B站从3.1万涨至7.6万；涨粉起色始于6月20日第一条外出拍摄的对话视频。
-- **直播项目**：视频号直播4-5场，平均每场在线人数5000+，前100人平均在线时长50分钟以上；因无课程产品，暂无法变现。
-- **账号变现**：课程变现评分7.5分（满分10分），其中0.5分为期待空间；重点项目未完成。
-- **商务部门**：2023年实打实项目约300万元，基本达到预期；另有入围等未计入的项目。
-- **项目交付**：全年项目未做砸过，客户满意度整体尚可；宁波城市项目、法院项目、警察学院驻场、财经宣传片等均完成交付。
+- **年度经营数据公布**：年终奖总额为226,000元；成本支出（人员工资、外援配音、字幕、租机器）390万元；利润率约24%或27%；最高工资（含年终奖）有2-3人达到20万元以上，平均到手工资1万多元
+- **人工支出变化**：2023年平时工资总额提高约25万元，年终奖比去年多13万或12万；干满一年的员工从去年的4-5人增加到今年的12人
+- **公司总量与结余**：公司总量提升、员工收入提升，但成本上升导致结余缩水，到账结余往下跑，另有百来万未收回
+- **老板个人收入**：老板个人收入比去年少约10万元，承担了约100万的亏损风险
 ## 数据与指标
-- **年终奖总额**：226,000元。
-- **成本支出**：人员工资、外援配音、字幕、租机器等实打实支出390万元。
-- **利润率**：约24%或27%，老板认为非常不可观。
-- **员工收入**：最高工资（含年终奖）有2-3人达到20万元以上；平均到手工资1万多元。
-- **人工支出变化**：2023年平时工资总额比去年提高约25万元；年终奖比去年多13万或12万。
-- **人员留存**：干满一年的员工从去年的4-5人增加到今年的12人。
-- **公司结余**：总量提升但成本上升，到账结余往下跑，另有百来万未收回。
-- **老板收入**：个人比去年少拿约10万元，承担了亏损100万的风险。
+- **视频号**：粉丝从3月1日的719人增长至8万，涨粉起色始于6月20日第一条外出拍摄的对话视频
+- **小红书**：粉丝从1月的2000+增长至6.4万
+- **抖音**：粉丝从2000+增长至5.7万
+- **B站**：粉丝从3.1万增长至7.6万
+- **账号变现**：课程变现评分7.5分（满分10分），其中0.5分为期待空间；变现重点项目未完成
+- **直播**：视频号直播4-5场，平均每场在线人数5000+，前100人平均在线时长50分钟以上
+- **商务部门**：实打实项目约300万元，加上入围等应更多
 ## 制度与流程
-- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元，今年约1000元；干满一年以一个月基本工资为基准；干得久且满意，预算可达大几万，实际拿到的一般为两三万。
-- **个人年终奖不一一公布**：以发到手的为准，口头提到的数字不作准。
-- **奖项评选标准**：共6人获奖、5个奖项，评选为2选1或3选1，强调公平、有竞争性；未获奖不代表能力不行，但至少证明不突出。
-- **颁奖侧重**：年终奖及奖项对后期执行部门有所侧重，老板表示这是唯一愿意解释的发放原因。
-- **加班补贴**：年终奖中考虑加班因素，补贴约一两千元。
-- **报销福利**：年会当天看电影或吃饭，一定额度内可报销，仅限当天。
+- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元，今年约1000元；干满一年以一个月基本工资为基准，表现好可更高；干得久且满意，预算可达大几万，实际拿到的一般为两三万
+- **个人年终奖数额**：不一一公布，以发到手为准
+- **奖项评选机制**：共6人5项奖，评选有竞争性，同级别框出2-3人，2选1或3选1；最佳新人奖含鼓励成分，后期三项奖完全出于肯定
+- **颁奖侧重**：年终奖及奖项对后期有所侧重，是老板唯一愿意解释的原因；拍摄人员收入不会比后期少
 ## 团队与人员
 ### 红叶子
-- **综合评价**：入职两三个月（10月入职、11月转正），政委给予非常高评价，认为很难招到既懂技术又懂英语、有把事情做好的精神头的人才；在工资表意见栏会认真写如何把项目做得更好的建议。
-- **获奖**：获最佳新人奖。
+- **综合评价**：入职两三个月（10月入职，11月转正），政委给予非常高评价，认为很难招到既懂技术又懂英语、有把事情做好的精神头的人才
+- **工作态度**：填工资表时在意见栏认真写如何把项目做得更好的建议
 ### 郭东辉
-- **运营能力**：有经验的运营，克服了本不应面对的困难，包括说服老板到外面拍摄、一人负责多平台运营；6月20日前老板曾10次提醒其出去找工作，其坚持不放弃并破釜沉舟说服老板外出拍摄，成为账号转折点。
-- **成长收获**：认知上学会说服自己、用数据支撑决策（每晚8-9点刷竞品直播间学习）；能力上学会开店、企业店等新事务；经验上总结出"破壳"方法论——找准一个点逐步解决问题。
+- **综合评价**：干满一年的运营，非常有经验，克服了本不应面对的困难；老板表示公司可能限制了他的发挥，应表示歉意
+- **账号运营**：负责多平台运营，6月20日前潘老师曾10次提醒其出去找工作，郭东辉坚持不放弃，说服潘老师外出拍摄后账号起色
 ### 刘腾宇
-- **职业性**：对老板和客户回复都非常专业，沟通表达能力强。
-- **专业性**：技术反馈好，宁波城市项目客户罗峰表示"如果不是你这个小姑娘做得好，你们做得这么慢，早投诉你们了"；重要活安排给刘腾宇后老板即放心。
-- **纪律性**：几乎没有迟到，请假严格按规定提前告知并安排好工作。
-- **年终奖**：因林海腾肯定，在既定标准上再拉一档；刚满一年但给老板感觉像干了5-6年的老员工，年终奖可能翻倍。
+- **综合评价**：评价最高，职业性、专业性、纪律性均为最好；按时完成交付，问题倒来倒去倒不到他头上；沟通专业，对客户回复得体
+- **客户反馈**：宁波城市项目客户罗峰向政委表示「如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了」
+- **年终奖**：刚满一年但给老板感觉像干了5-6年的老员工，年终奖会让人惊喜，可能翻倍
 ### 欧阳小元
-- **工作态度**：认真，有学习能力，技术水平有进步。
-- **获奖**：获最佳进步奖，技术进步明显跑了一截。
+- **综合评价**：刚满一年，工作态度认真，技术水平有学习能力，进步明显；沟通能力需再爬坡
+- **获奖**：获最佳进步奖
 ### 徐艺玲
-- **工作质量**：一遍过的非常多，仔细认真挑不出毛病；技术有进步，原先只能剪课程，今年剪宣传片类像模像样。
-- **客户反馈**：杨晶项目其他人做不了，客户点名"还是让那个小姑娘来做"。
+- **综合评价**：干得稍久的员工，一遍过的次数非常多，仔细认真挑不出毛病；技术层面有进步，原先只能剪课程，今年剪宣传片类也像模像样
+- **客户认可**：杨晶项目其他人做不了，徐艺玲做完后客户说「你还是让那个小姑娘来做」
 ### 张文倩
-- **综合能力**：编导岗位，需要沟通能力和专业水平；表现高于老板期待，宁波等难活本以为干不了但完成了。
-- **待提升**：因年龄和工作年限，经验和职场感觉有所欠缺。
+- **综合评价**：编导岗位，综合能力强（沟通+专业），表现高出老板期待；宁波等难活本以为干不了但完成了
+- **待提升**：因年龄和工作年限，经验与职场老人有差距
 ### 市井
-- **技术标杆**：后期方面技术标杆，最好的没有之一；能胜任更高品质的工作，参与项目沟通会议。
+- **综合评价**：后期技术标杆，最好的没有之一；品质上依然最高
+- **获奖**：获后期独挡一面奖，能完美胜任课程、微电影、MV、快剪等各类后期
 ### 钱德峰
-- **拍摄贡献**：元老级人物，后半年拍摄密集，两个月连轴转没有一天休息；除拍摄外还安排拍摄人员。
-- **额外贡献**：主动建议办停车券、设备更新等运营层面事项，关心公司发展。
+- **综合评价**：元老级人物，后半年拍摄密集，两个月连轴转没有一天休息；除拍摄外还安排拍摄人员，操心较多
+- **额外贡献**：主动建议办停车券、设备更新等运营层面事项，非本职工作但关心公司发展
 ### 徐武安
-- **驻场表现**：在警察学院驻场，一人孤苦伶仃非常辛苦；客户从最初认为经验欠缺到后来觉得"挺灵的"，反馈不错。
-- **技术水平**：拍摄和后期技术过关，拍摄水平好于后期。
+- **综合评价**：灵光、眼里有活，驻场警察学院孤苦伶仃非常辛苦；拍摄技术水平好于后期技术水平
+- **客户反馈**：刚去时被认为经验欠缺，后来反馈「挺灵的」
 ### 宋俊逸
-- **编导能力**：入职两三个月，第一个活是宁波两分钟小宣传片，收到要求后很快写好文稿，老板评价"行家一出手便知有没有"；后续监狱、财经等项目未出任何问题，完全放心。
+- **综合评价**：入职两三个月，编导职位；第一个宁波两分钟宣传片任务，发来文稿后老板觉得「行家一出手便知有没有」，效率高
+- **交付情况**：监狱、财经等项目未出现任何问题，交给其完全放心
 ### 张扬
-- **综合评价**：公司邀请来的人才，入职半年左右，职业态度和工作能力有目共睹，基本达到期待；老板认为2023年干到最有价值的事就是招他进来。
-- **获奖**：获最佳新人奖。
+- **综合评价**：公司邀请来的人才，来了半年左右，职业态度和工作能力有目共睹，基本达到期待；老板认为2023年最有价值的事就是招其进来
+- **获奖**：获最佳新人奖
 ### 林海腾
-- **运营作用**：对运营层面有重要作用，上传下达，传达员工声音；后期安排工作繁重。
-- **获奖**：获特别贡献奖，奖金为单项奖中最多；因辛苦程度最大、操心最多、承担救火和上传下达角色。
+- **综合评价**：对运营层面有重要作用，上传下达；后期安排是繁重的活
+- **获奖**：获特别贡献奖，奖金为单项奖中最多；辛苦程度最大，半夜或周末被侵占最多，负责救火、沟通协调
 ### 李国宇
-- **拍摄水平**：公司内算比较高，能胜任稍高难度的拍摄。
-- **后期灵性**：剪理工项目第一遍乱七八糟，经沟通后完美交差，能听懂能进步。
+- **综合评价**：干满一年，拍摄水平在公司算较高，能胜任稍高难度工作；后期有灵性，能听懂指导
+- **待提升**：沟通能力需加强
 ### 张启
-- **商务表现**：干了一年的商务，表现高于老板预期；性格外向，有主观能动性，主动联系客户打电话。
-- **支持需求**：老板支持较少，几乎没什么项目，后续将给予更多支持和帮助。
-### 李不续
-- **后期能力**：获后期独挡一面奖，能完美胜任课程、微电影、MV、快剪等各类后期；政委评价高，承担了难以沟通课程的沟通角色，有时搞到半夜。
-### 后期团队整体
-- **技术进步**：后期人员之间明确分级今年模糊化，效率整体差不多，制作能力提升。
-- **工作强度**：后半年基本都在加班，包括晚上和周末；高强度下仍保证质量，有怨言但继续干，体现职业操守。
-## 年度总结与表彰
-- **年度总结**：2023年公司总量提升，员工拿到钱提升，成本也往上跑；总量提升是能开年会、发年终奖的最大原因。
-- **颁奖仪式**：今年认真对待仪式感，证书为皮质、40元一本含设计费，字体认真校对；另有洗手包（值七八十元）未寄到。
-- **奖项设置**：最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李不续）、最佳员工奖（刘腾宇）、特别贡献奖（林海腾，奖金最多）。
-- **抽奖福利**：共15个奖品，包括价值约180元的充电宝、79元观影券、49元观影券、30元观影券、价值七八十的洗头膏；老板另写了一个"发100块红包"的奖；林海腾发200元红包在群里。
+- **综合评价**：干了一年的商务，表现高于预期；以为害羞实际外向，有主观能动性，主动联系客户打电话
+- **支持情况**：老板支持较少，几乎没什么项目，后续会考虑给予更多支持
+## 年度总结、奖项与福利
+- **最佳新人奖**：颁给红叶子、张扬，各含红包
+- **最佳进步奖**：颁给欧阳小元
+- **后期独挡一面奖**：颁给市井，政委搜了好久名字，为独有奖项
+- **最佳员工奖**：颁给刘腾宇，含金量最高，老板与政委认真讨论、达成一致
+- **特别贡献奖**：颁给林海腾，奖金为单项奖中最多
+- **证书制作**：皮质证书40元一本（含设计费），字体认真校对，不掉色掉粉
+- **抽奖福利**：15个奖品，含充电宝（价值约180元）、观影券（价值30元）、洗头膏（价值七八十元，未寄到）；老板另写了一个100元红包的奖
+- **报销福利**：当天看电影或吃饭在一定额度内可报销，仅限当天
 # 亮点事项
-## 账号运营破局与增长
-- **粉丝量级跃升**：郭东辉负责的短视频账号在2023年实现多平台大幅增长，视频号粉丝从3月1日的700人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，增长拐点均始于6月20日第一条外出拍摄的对话视频。
-- **破局关键动作**：6月20日前潘老师已10次提醒郭东辉「出去找工作」，项目濒临放弃；郭东辉因收到其他公司邀约而**以破釜沉舟的心情极力说服潘老师到户外拍摄**，潘老师同意后恰逢新同事加入，项目得以坚持并迎来转折。
-- **坚持与自我说服**：郭东辉认为「说服自己是最难的」，通过自我说服坚持推进项目；其「破壳」经验为**找准一个点集中突破**（如鸡蛋轻敲桌面即碎），而非四面用力。
-- **数据驱动决策**：郭东辉每晚8–9点抽一小时刷竞品直播间（侃哥、巧克力、克瑞斯金等英语老师），研究其内容与互动方式，所有内容决策均有数据支撑而非凭空冒出的想法。
-- **外部认可佐证**：老板转述同行（卖虾、卖螃蟹的运营者）评价，惊讶于团队「居然能做这么久」，按他们的经验这种状况早已放弃；老板表示「因为有这样的员工，我要把这个事搞成了才能对得起人家」，员工表现反向给予老板信心。
+## 账号运营突破与坚持
+- **粉丝量级跃升**：视频号粉丝从3月1日的700人增长至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，**全部平台自6月20日第一条外拍对话视频起出现转折**。
+- **破局关键动作**：运营郭东辉在潘老师先后**10次**提醒放弃该项目的情况下坚持不放弃，以破釜沉舟的心情极力说服潘老师到室外拍摄，恰逢新同事加入，项目得以延续并实现增长。
+- **直播初步验证**：视频号直播4-5场，平均在线人数达5000+，前100名观众平均停留50分钟以上，为后续变现打下基础。
+- **外部认可佐证**：同行运营者（卖虾、卖螃蟹的商家）对团队能坚持这么久表示惊讶，认为按常规状况早该放弃。
 ## 员工表现超出预期
-- **刘腾宇（最佳员工奖）**：入职刚满一年却给老板「干了5、6年老员工」的错觉，职业性、专业性、纪律性均为最高评价；沟通上「他说的就是我说的，比我说的还行」，老板在群里着急私聊指导的情况在他身上从未发生；因林海腾的高度肯定，年终奖在既定标准上**再拉一档**，老板称「应该会让你比较惊喜，可能还会翻倍」。
-- **红叶子（最佳新人奖）**：入职两三个月即获政委「非常高的评价」——「很难招到这样的一个人才，既懂技术又懂英语，而且有把事情做好的精神头」；在工资表意见栏主动写如何把项目做得更好，而非像其他人只写「把报销和工资一起发」。
-- **张扬（最佳新人奖）**：公司主动邀请的人才，老板称「2023年干到最有价值的一件事就把他招进来」；其到来带来职业态度与工作能力上的改变，基本达到期待；除剪辑外还能做三维包装，而往年二维三维均外包，有望内部解决。
-- **宋俊逸（编导）**：入职两三个月，老板安排第一个宁波两分钟宣传片任务，要求发出后不久即交回文稿，老板评价「行家一出手便知有没有」，后续监狱、财经等项目均未出问题，「交给他是完全放心的」。
-- **张文倩（编导）**：表现高于老板期待，宁波等老板原以为会黄的难活均能完成，「出乎我的意料」；老板评价其岗位需综合沟通能力与专业水平，非灵光之人做不了。
-- **欧阳小元（最佳进步奖）**：技术进步「明显的跑了一截」，老板强调「进步这个东西不是所有人都有的」，今年有意识让其尝试更多类型片子，均能胜任。
+- **刘腾宇获最高评价**：老板称其为评价最高、没有之一，职业性、专业性、纪律性俱佳；客户（宁波城市项目）反馈「如果不是你这个小姑娘做得好，你们做得这么慢，早投诉你们了」；重要活安排给刘腾宇后老板可直接放心遗忘；因林海腾大力肯定，年终奖在既定标准上**再拉一档**，老板预计「可能还会翻倍」。
+- **红叶子获政委高度评价**：政委（平时相对严苛）评价「很难招到这样的一个人才，既懂技术又懂英语，而且有把事情做好的精神头」，在工资表意见栏主动写如何把项目做得更好。
+- **张扬获老板最高认可**：老板称「2023年干到最有价值的一件事就是把他招进来」，其职业态度与工作能力基本达到期待，且能做三维（往年二维三维均外包），段位让人惊喜。
+- **宋俊逸首活即证能力**：入职两三个月，老板安排宁波两分钟宣传片，文稿发来后老板判断「这个人是对的」，后续监狱、财经等项目未出任何问题，完全放心。
+- **张文倩完成高难度项目**：老板原以为宁波类项目可能黄掉，但张文倩完成且超出期待，被认为综合能力（沟通+专业）要求高的岗位做得「出乎意料」。
+- **欧阳小元获最佳进步奖**：技术进步「明显跑了一截」，老板强调「进步不是所有人都有的」，并寄语保持热爱与好奇。
 ## 仪式感建设与激励创新
-- **奖项体系从无到有**：去年李海腾建议公司欠缺仪式感，今年老板认真对待，设立**最佳新人奖、最佳进步奖、后期独挡一面奖、最佳员工奖、特别贡献奖**共5项6人，评选标准为2选1或3选1，强调公平有竞争性。
-- **用心准备细节**：证书为皮质、40元一本含设计费，老板「连字体都认真对过」，特意要求不掉色掉粉；个人评价台词「每一句都认真想过，不是现场发挥」；年终奖总额226,000元，从公司体量而言「比较有诚意」。
-- **特别贡献奖授予林海腾**：奖金为单项奖中最多，因其辛苦程度最大（半夜、周末被侵占最多）、最操心（执行层面救火、上传下达），对运营有重要意义。
-- **加班补贴纳入年终奖**：老板与政委商量年终奖时，对加班「不能说是奖励，就是再补贴一部分」，考虑一两千元额度。
-## 商务拓展与外部认可
-- **商务部门实打实项目约300万元**：老板梳理后认为整个部门实打实项目在300万左右，若计入入围等项目则更多；张启作为干满一年的商务，表现高于老板预期——原以为害羞内向，实际「玩得挺开、挺外向」，且**有主观能动性**，未安排也会主动联系客户打电话。
-- **客户正向反馈**：宁波城市项目客户罗峰向政委表示「如果不是你这个小姑娘做得好，你们做得这么慢，早投诉你们了」，直接印证刘腾宇的交付质量。
+- **首次正式颁奖**：增设最佳新人奖、最佳进步奖、后期独挡一面奖、最佳员工奖、特别贡献奖共5项6人，源于去年李海腾建议公司欠缺仪式感；老板称今年**非常认真对待**，奖项评选经与政委认真讨论，2选1或3选1竞争性评选。
+- **证书细节用心**：皮质证书40元一本（含设计费），老板亲自核对字体，选用「苍耳青和」字体，明确要求不掉色掉粉。
+- **年终奖总额提升**：年终奖总额226,000元，比去年多13万或12万；干满一年员工从去年4-5人增至今年12人；最高收入（含年终奖）2-3人达20万以上，平均到手工资1万多元。
+- **加班补贴纳入考量**：与政委商量年终奖时，对后半年高强度加班（含晚上、周末）在年终奖基础上**再补贴一两千元**，作为对辛苦的认可。
+## 成本优化意识萌芽
+- **内部拍摄可行性被提出**：钱德峰指出部分外援工作（如简单按机位、保证机器不关机）公司内部即可完成，但「连这样的人公司都凑不出来」；外援拍摄与内部人员拍摄**两边价格差很多**，建议后期人员尝试参与拍摄，既提升收入也增加体验。
+- **老板回应并定调**：认可拍摄性价比高，未阻止任何人参与，期待明年大家都能参与拍摄，称这对个人市场价值也是提升。
 # 不足事项
-- **成本控制非常差**：2023年实打实花出去的钱（含人员工资、外援配音、字幕、租机器）达390万元，利润率仅约24%或27%，老板明确称这是公司最大的问题；若当年没有增量，成本控制又是这个状况，年会都不会开。根因：**老板对成本关心或关注不够，不够雷厉风行，出现问题未及时解决**。
-- **公司结余缩水**：总量在提升、员工拿到钱在提升，但成本也在往上跑，公司结余到账往下跑，还有百来万没收回来，实际是稍微缩水的。根因：成本上升速度超过总量提升带来的结余。
-- **老板个人收入下降**：老板个人比去年少拿约10万元左右，且承担了亏损100万的风险。根因：公司结余缩水直接传导至老板个人收入。
-- **账号变现重点项目未完成**：账号变现课程评分7.5分（满分10分），其中0.5分是期待空间，重点项目可以说没有完成。根因：账号目前没有课程，无法进行变现。
-- **直播无法变现**：视频号直播了4-5场，平均在线人数5000+，前100人平均在线时长50分钟以上，但因为没有课程，所以无法变现。根因：直播内容与人数已具备条件，缺课程这一变现载体。
-- **后期人员不足导致加班多**：后半年基本都在加班，很少正常休息，高强度工作下大家有怨言但仍接着干。根因：**老板没有及时招更合适或更合适人数的人员**——商务给活是第1信号，业务断断续续产生错觉，认为不需要招这么多人，但平时积累的人脉资源又不确定，属于判断失误。
-- **拍摄外援成本偏高**：请了很多天外援，但有些活公司自己人内部就可以搞定（如上午谁有空去按个机位、让机器不关机），公司却凑不出这样的人；外援价格与内部人员拍摄价格差很多。根因：后期人员活多且麻烦，加上安排不开，导致依赖外援。
-- **商务部门招人判断失误**：商务部门实打实项目约300万左右，但老板承认对商务部门给予的支持、管理或关心不够。根因：老板对商务部门支持少，张启几乎没有项目，老板只是帮他聊了聊或打理。
-- **老板对员工关心或关注不够**：老板自述对员工关心或关注不够，不够雷厉风行，出现问题未及时解决；对商务部门给予的支持、管理或关心不够，明年会反思这个问题。根因：老板管理方式问题。
-- **拍摄与后期年终奖侧重不一致**：年终奖及奖项发放侧重于后期，拍摄人员拿到的比后期少一截，老板称这是唯一愿意解释的原因。根因：老板主观意志决定，但承认拍摄辛苦程度高。
-- **部分员工沟通能力待提升**：欧阳小元沟通能力可能要再爬坡；李国宇沟通能力有问题且很严重；张文倩因年龄和工作年限问题，经验或感觉上职场老人有所欠缺。根因：个人能力发展阶段差异。
-- **员工自我评价未达预期**：张启自评2023年没达到自己的预期，效率、时间、项目上对同事和甲方的沟通做得不太好。根因：个人效率与时间分配、沟通方式问题。
+- **成本控制极差**：2023年实打实花出去的钱（含人员工资、外援配音、字幕、租机器）达390万元，利润率仅约24%或27%，老板直言“非常不可观”。根因：**老板对成本关心或关注不够，不够雷厉风行，出现问题没有及时解决**，老板自认“最大的癌症的问题，根源的问题就是老板的问题”。
+- **公司结余缩水**：虽然总量提升、员工收入提升，但成本往上跑，公司结余到账往下跑，且还有百来万没收回来，实际结余“稍微缩水”。根因：成本上升幅度超过总量提升带来的结余空间。
+- **老板个人收入下降**：老板自述“我们每个人会比去年少拿个10万块钱左右”，且公司承担了亏损100万的风险。根因：成本控制不力叠加未收回款项，压缩了老板个人收益。
+- **账号变现重点项目未完成**：短视频账号粉丝大幅增长（视频号从700涨到8万，小红书从2000+涨到6.4万，抖音从2000+涨到5.7万，B站从3.1万涨到7.6万），但账号变现课程评分仅7.5分（满分10分），老板明确“重点项目的话可以说是没有完成”。根因：账号起步艰难，6月20日之前老板曾10次提醒运营“出去找工作”，项目差点放弃；变现能力尚未建立，直播虽场均5000+人但“没有课程，所以说他是可以进行变现的”尚未落地。
+- **加班严重、休息时间被侵占**：后期部门后半年基本都在加班，晚上、周末都在赶工，很少正常休息。根因：**人不够是最大因素**——老板承认“没有及时招更合适或更合适人数的人员来做这个事儿”，商务业务断断续续产生，给人“不需要招这么多人”的错觉，但平时积累的人脉资源又不确定，导致判断失误。
+- **外援成本高但内部无人可用**：拍摄请了大量外援，成本很高，但部分工作公司自己人内部就可以搞定（如“上午谁有空谁去一下，按个机位，只要让机器不关机就ok”），实际“这样的人我们公司都凑不出来”。根因：后期人员活多且忙，抽不出人手；老板也承认部分外援是“我们技术水平达不到”所致。
+- **拍摄与后期收入不平衡**：老板明确“拿到了钱，其实后期要比前期少一截的”，且年终奖和奖项“侧重于后期”。根因：老板主观意志决定，但承认这是“唯一愿意解释的一点”，希望员工理解。
+- **员工拒绝拍摄安排**：老板指出安排拍摄时，有员工直接说“我没空”，老板认为“这个是非常不职业的”。根因：员工缺乏职业意识，老板要求“如果领导问到你应该起码解释一下我手头上忙的东西，或者说你勉为其难安排一下”。
+- **商务部门支持不足**：老板承认“我们做老板来说，给他的支持比较少，他几乎没有什么项目，我们就帮他聊了聊，或者是帮着他走走打理”。根因：老板对商务部门“给予的支持，或者管理或者是关心其实是不够的”，明年会反思这个问题。
+- **员工自我评价未达预期**：后期员工自述“2023年就是我自己对我自己的预期的话，我感觉年终对我自己来说，我感觉是没达到我自己的预期的”，原因包括效率、时间、项目上对同事和甲方的沟通做得不太好。
+- **个别员工沟通吃力**：张文倩反映法院项目“虽然是做完了，但是我同学跟他们沟通上会比较吃力”，因为对方“总是在踢皮球”，标准不明确。
 # 改进计划
-## 成本控制与经营风险
-- **针对成本控制差、利润率仅约24%或27%的问题**：老板表示明年开会时再讨论成本控制事宜，未给出具体方案。
-- **针对公司结余到账往下跑、有百来万没收回来的问题**：老板未提出具体追收或改善措施，仅承认这一现状。
-- **针对老板个人比去年少拿约10万、承担亏损100万风险的问题**：老板未提出个人收入调整或风险应对计划，仅说明现状。
-## 管理方式与人员配置
-- **针对老板对员工关心或关注不够、不够雷厉风行、出现问题未及时解决的根因**：老板明确表示明年会反思这个问题，并计划给予员工更多支持、管理和关心。
-- **针对后期人员不足导致加班多的问题**：老板承认是判断失误，本质上是没有及时招合适或足够数量的人员，但未给出明年具体的招聘计划或人数目标。
-- **针对商务部门招人判断失误导致人不够的问题**：老板承认因业务断断续续产生错觉，未及时招人，但未提出明年具体的招聘安排。
-## 短视频账号与变现
-- **针对账号变现重点项目未完成、直播无课程无法变现的问题**：老板表示明年期待账号能开始变现，并会投入更大精力、给予足够重视来做这个事情。
-- **针对短视频账号运营中说服与坚持困难的问题**：运营郭东辉提出，说服自己是最难的，最大敌人是自己，需要坚持把事情做下去。
-## 拍摄能力与人员参与
-- **针对外援拍摄成本高、公司内部凑不出人按机位的问题**：员工钱德峰建议尝试让公司内部人员参与拍摄，一方面提升收入，另一方面体验拍摄工作；老板回应称期待大家都能参与拍摄，明年会往这个方向靠，希望每个人都能应付基本拍摄。
-- **针对员工直接回复“没空”不参与拍摄、被认为不职业的问题**：老板指出，如果领导问到，应起码解释手头忙的东西或勉为其难安排一下，直接说没空是非常不职业的。
-## 员工个人提升方向
-- **针对刘腾宇综合后期技术水平提升空间的问题**：老板提出更高期待，希望其综合后期技术水平更高，能完美胜任各种类型的工作。
-- **针对欧阳小元沟通能力需提升的问题**：老板中肯评价其沟通能力需要再爬坡，同时希望其保持热爱与进步。
-- **针对李国宇沟通能力有待提升的问题**：老板指出其沟通能力有问题且很严重，但未给出具体改进方法。
-- **针对张文倩因年龄和工作年限导致经验欠缺的问题**：老板认为其灵光性强、能进步，可从公司角度发挥更大价值，未给出具体培养计划。
-- **针对钱德峰执行能力需提升的问题**：老板提出更高期待，希望其有更强的执行能力，包括项目执行和沟通谈判方面。
-- **针对市井需解决部分较难问题**：老板期待其能参与解决一部分公司认为比较难的问题。
-## 商务支持与组织协调
-- **针对商务张启项目支持少、老板帮助有限的问题**：老板表示后面会考虑给予更多支持和帮助，包括帮着聊项目、打理事务。
-- **针对执行部门工作忙碌、休息时间被侵占的问题**：老板期待明年能更多进行组织协调，提高效率，提升大家工作开心程度，尽可能少侵占休息时间。
-- **针对商务部门整体结果基本达标但需提升的问题**：老板未给出具体改进措施，仅表示明年会继续关注该部门。</t>
+## 成本控制与经营改善
+- **针对成本控制差、利润率仅24%或27%的问题**：老板表示明年开会时再讨论成本控制事宜，未给出具体方案或责任人。
+- **针对公司结余缩水、有百来万未收回的问题**：老板提及有百来万未收回，但未给出明确的回款计划或时间表。
+## 管理改进
+- **针对老板管理不足、对员工关心或关注不够、不够雷厉风行、出现问题未及时解决这一成本问题的根源**：老板明确表示明年会反思这个问题，并计划给予员工更多的支持、管理和关心。
+- **针对商务部门支持不足的问题**：老板表示后面会考虑给商务部门员工（如张启）更多的支持和帮助，包括协助洽谈项目。
+## 拍摄与人员安排
+- **针对外援成本高、部分拍摄工作内部人员即可完成但无人手的问题**：钱德峰建议尝试让公司内部人员参与拍摄，以提升收入并体验工作；老板回应称期待大家都能参与拍摄，明年会往这个方向靠，希望每个人都能参与。
+- **针对员工以「没空」等理由拒绝拍摄安排的问题**：老板指出直接说「没空」非常不职业，要求员工在领导询问时应解释手头工作或勉为其难安排，此事项明年再议。
+## 短视频账号发展
+- **针对短视频账号尚未变现的问题**：老板表示明年期待账号能开始变现，并会投入更大的精力、给予足够的重视。
+## 后期部门工作负荷
+- **针对后期部门加班严重、人不够是最大因素的问题**：老板承认未及时招聘合适或足够人数的人员是判断失误，但未给出明年的具体招聘计划或人数目标。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>93.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/7730</t>
+          <t>24562/6443</t>
         </is>
       </c>
     </row>
@@ -2092,72 +2073,100 @@
       <c r="C5" t="inlineStr">
         <is>
           <t># 全文摘要
-本次专项讨论会由办事处组织，小区业委会代表与物业方就服务质量、物业费欠费及业主大会召开等事宜进行协调。业主自发接龙约200位业主，主要诉求为召开业主大会表决物业去留；物业方称未接到沟通，且已决定本月起诉业委会，双方未达成一致。会议围绕业主大会召开与物业去留、小区问题清单与物业回应、物业费欠费与亏损三个板块展开。业主代表列举小区10条问题，物业方逐条回应，称部分问题属地产责任、费用不足或超出服务范围，双方对责任归属分歧严重。物业方宣布已与集团法务沟通，本月将起诉业委会，并称起诉期间无法更换物业公司；业主方决定正常推进业主大会召开。关键数字：业主欠物业费170多万、园区年收入100余万、人工成本100余万、维修人员从5人减至2人。双方就诉讼期间能否召开业主大会、欠费与服务改善先后等问题未达成一致，会议未形成调解结果。
+本次专项讨论会由办事处组织，业主代表、业委会工作组与物业方就小区服务问题及业主大会召开事宜进行协调。业主方列举10条长期未解决的服务问题（入户门柱灯、水系、监控、绿化、围墙、民生配套、雨水倒灌、人员配备等），要求召开业主大会表决物业去留；物业方逐条回应，称资金困难、部分问题属地产责任，并宣布本月起诉业委会。双方未达成一致，业主方决定正常推进业主大会。物业方称业主欠费170多万，回款40万可修部分问题；年收入100来万，人工成本100多万，每年亏损；部分问题属地产前期配套或红线外责任，地产公司已申请破产。业主方认为服务不达标导致拒缴，形成恶性循环，并称可能集体起诉要求返还部分物业费；物业方称起诉期间无法更换物业公司。
 # 分段速览
-## 00:10-05:04 开场与背景讨论
-会议开场，发言者2与发言者1、3、4围绕小区物业费、供暖开户费及园区验收问题展开讨论。发言者2称园区从建设至今未验收，供暖开户费应由地产出资并交接给供暖公司，但至今未完工；开发商已交配套费，但费用去向不明。发言者4提到业主买房满怀希望不愿退房，发言者2称二期补助约29%，并提及业主自发组织交费约400元、涉及13万款项及2023年收费问题。
-## 05:04-10:14 业主大会筹备讨论
-发言者2与发言者4、5讨论业主大会筹备事宜。发言者4称业主自发接龙约200来位业主，主要议题是召开业主大会表决物业去留；发言者2质疑接龙程序，称未参与、不了解议题。发言者5提到接龙业主心声包括要求整改小区问题、达不到效果可招标换物业。发言者2强调成立业委会应坦诚相待、不暴露敌对情绪，并提及配电室三级问题需排查。
-## 10:14-14:28 业委会工作群与接龙来源
-发言者2询问业委会工作群数量，发言者4称工作组群1个、准业主群5个共6个群，由筹备组6人各联系一部分业主；接龙群为交房时老邱哥建的业主群，已有5、6年历史。发言者2质疑接龙程序合法性，称未参与、无法讨论200人接龙结果，强调召开业主大会需有程序依据。
-## 14:28-18:01 业主大会程序与议题
-发言者5总结接龙业主心声：要求开会、整改小区问题，整改不了可招标换物业，原物业也可投标。发言者2强调召开业主大会需事先与物业沟通，但物业未接到任何通知，质疑接龙有组织性。发言者4称业委会意思不是让所有业主到现场，而是通过表决决定物业去留。
-## 18:01-21:23 物业方宣布起诉
-发言者2代表物业方郑重声明：鉴于双方存在违法情况，已与集团法务沟通，本月将起诉业委会；欠费人员不能成为业主代表，将依法追究责任。发言者2称已在业主群掌握证据，上午9:52与高级人民法院通话，也与滨城区人民法院沟通，将起诉业委会及保洁业主代表，起诉过程可能影响个人经营。
-## 21:23-23:02 会议性质确认
-发言者5称业主大会开与不开是必须的事，今天先讨论问题能否改善；发言者4称能改善早改善了。发言者2强调会议严肃性，要求记录问题并讨论整改可能性。发言者3称问题没解决业主不愿交物业费，物业没钱导致情况越来越糟，形成恶性循环。
-## 23:02-31:22 业主列举10条问题
-发言者4逐条列举小区问题：①入户庭院门柱灯从未开启；②内部水系从未运行；③售楼处迎宾水系从未开启；④监控几乎全部损坏，上个月进贼派出所和刑警未获监控数据；⑤监控室24小时值班及门铃一键直达服务荒废；⑥绿化维护差，去年死了很多树，物业管家称等明年看能否发芽；⑦北边围墙用烂铁皮挡着且有缺口，社会人员可随意进出，物业称已定制围挡但证实未定制；⑧快递柜、直饮水机、宽带、暖气开户等民生配套无进展；⑨雨水倒灌问题从2019年至今未解决；⑩物业人员配备不足，办公室从近10人减至4人，维修人员从5人减至2人。
+## 00:10-05:37 开场与费用问题讨论
+会议开场，发言者2与发言者1、发言者3就小区供暖开户费、配套费缴纳情况展开讨论。发言者2指出园区从建设到后期从未验收，开户费应由地产出资并将管道交接给供暖公司，但至今未完工，导致责任归属不清。发言者3确认相关费用已交清，发言者2补充称开发商将费用交入其公司，具体去向不明。发言者2还提及业主退费、工资比例等话题，但表述零散，未形成明确结论。
+## 05:37-10:14 业主诉求与物业现状
+发言者4提出业主买房满怀希望、不愿退房，发言者2回应称一期结算时按平方点计算，二期补助可达29%。发言者2提到有热心业主自发组织收费，涉及3万元及400元费用，但未推进。发言者4补充称二期三期交费业主合计约20来户。发言者2表示物业费收缴不足50户难以维持运营，并提及配电室三级管理问题，强调需坦诚相待、共同商量解决。
+## 10:14-14:28 业委会成立与群组情况
+发言者2强调成立业主委员会应保持良好态度、不暴露敌对情绪，任何人不应有私心。发言者4介绍小区业主自发组织接龙，约200名业主支持召开业主大会，并指出业委会或业主无权单方面撤换物业，需业主大会表决。发言者2询问工作群数量，发言者4回应称业委会工作组仅一个群，准业主分5个群，筹备组6人各联系一部分；最早的业主群由老邱哥建立，已有5、6年历史。
+## 14:28-17:53 业主大会程序讨论
+发言者2质疑接龙程序，认为讨论需有明确结果，不应失控。发言者5总结接龙业主心声：一是要求整改小区存在问题，二是整改不了则考虑更换物业，原物业也可参与投标。发言者5提及业主群中列出11个问题。发言者2强调召开业主大会前应与物业公司沟通，但物业方未接到任何通知，认为接龙有组织性，物业方未参与议题制定。
+## 17:53-21:23 物业方宣布起诉
+发言者2郑重声明，鉴于双方存在违法情况，已与集团法务沟通，本月将正式起诉业委会，并称欠费人员不能成为业主代表。发言者2表示已在业主群掌握证据，上午与高级人民法院、滨城区人民法院均有沟通记录，将起诉业委会及保洁业主代表，起诉过程可能影响个人经营。
+## 21:23-30:53 业主列举10条问题
+发言者4逐条列举小区长期存在的问题：①入户门柱灯从未开启；②内部水系从未开启；③售楼处迎宾水系从未开启；④监控几乎全部损坏，上月进贼未获取数据；⑤监控室24小时值班及一键直达功能荒废；⑥绿化维护不足，去年死树多棵；⑦北边围墙用烂铁皮遮挡且有缺口，存在安全隐患；⑧快递柜、直饮水机、宽带、暖气开通等民生问题无进展；⑨雨水倒灌问题自2019年存在未解决；⑩物业人员从办公室近10人减至4人，维修人员从5人减至2人。
 ## 31:22-38:01 物业方逐条回应
-发言者2逐条回应：①门柱灯因能耗成本高未开启，业委会曾承诺协助收费后修复；②水系从交付起存在质量问题，属地产维修责任；③监控损坏因费用超运营承担，园区年收入100余万、人工成本100余万，每年亏损；④民警进园区时物业已第一时间将监控画面截取给派出所和刑警；⑤绿化死亡因业委会10月成立后已入冬季，换树责任难定；⑥北边围墙属红线外且涉及违建，物业有权不处理，曾协调厂家定做但因费用高未成；⑦民生配套属地产前期配套，开通费用由业主承担；⑧雨水倒灌属地产设计问题，超出物业解决范围；⑨人员配备不足因地产补亏款未结账，项目20来人年成本100多万。
-## 38:01-46:14 双方激烈交锋
-发言者4反驳物业方，称物业服务无滞后性，不能先收钱再服务；门柱灯、水系、监控等问题从交房至今是时序性问题，非物业来后才出现。发言者2称今天目的是协调业委会问题，并非要求换物业。发言者4称已无讨论必要，基本定下召开业主大会、决议换掉物业。发言者2称起诉期间无法更换物业公司，发言者4称业委会成立之日已自动解除物业合同关系。双方就围栏定制、半热带安装等承诺争执，发言者4称物业经理曾说不交物业费就上门吃饭。
-## 46:14-53:01 欠费与起诉争论
-发言者3称问题没解决业主不愿交物业费，物业没钱导致情况越来越糟。发言者4提出业主可能集体起诉物业要求返还部分物业费。发言者7称上午已给求助人打电话，又给集团法务打电话，集团法务今天操作手续，业主群动态已截屏保存。发言者8质疑物业窥探业主隐私，称可反诉。发言者4称物业经理曾说不交物业费就上门吃饭，发言者7否认并要求提供录音。
+发言者2逐条回应：①门柱灯因能耗成本过高无法运营，业委会曾承诺支持缴费后修复；②水系存在严重质量问题，属地产配套未完成；③监控维修因费用超出运营承担，园区年收入100来万、人工成本100多万，每年亏损；④监控画面已第一时间提供给警方；⑤绿化问题因业委会10月才成立，冬季无法更换；⑥北边围墙属红线以外且涉及违建官司，物业无责处理；⑦民生配套属地产前期配套；⑧雨水倒灌属地产设计问题；⑨人员配备不足因地产补亏款未结账。
+## 38:53-46:14 双方争执激化
+发言者4反驳称物业服务无滞后性，问题从交房至今一直存在，并非物业方近期资金困难才出现。发言者2坚持走法律程序，称诉讼期间无法召开业主大会。发言者4表示会议无继续必要，基本决议是换掉物业，并称业委会成立之日已自动解除物业合同关系。发言者2要求先结清费用，双方就围栏定制、半热带安装等承诺未兑现问题争执。
+## 46:59-53:01 恶性循环与反诉表态
+发言者3指出无钱无法整改、业主不愿缴费形成恶性循环，区领导也难以解决。发言者4提出可能集体起诉要求返还部分物业费。发言者8质疑物业窥探业主隐私，表示将反诉。发言者7称已与集团法务沟通，业主群动态已截屏留证。发言者5建议业主大会开与不开都应推进，需与物业打招呼明确议题。
 ## 53:01-01:03:16 调解失败与会议结束
-发言者3建议双方冷静、往好方向发展，称办事处领导牺牲时间是为了小区好。发言者3要求物业反思为何前几年物业费交得齐、现在不行，称矛盾越积越尖锐。发言者7称业主欠物业费170多万，回款40万可修部分问题，地产公司已申请破产。发言者3称服务好是交费前提，发言者7称公司一直亏损、今年亏损拉大。发言者4称正常推进业主大会，不再与物业沟通。发言者2称今天结果不好，未解决实质性问题，会议结束。
+发言者3建议双方冷静、向好的方向发展，物业应拿出真实行动赢得业主认可。发言者7表示公司入不敷出，业主欠费170多万，回款40万可修部分问题，地产公司已申请破产。发言者3指出服务好是缴费前提，矛盾越积越深更难解决。发言者4表示将正常推进业主大会，发言者2称会议未解决实质性问题，双方未达成一致，会议结束。
 # 要点梳理
-## 业主大会召开与物业去留
-- **业主诉求**：业主自发组织接龙，约200来位业主参与，主要议题为召开业主大会表决物业去留。
-- **群组情况**：业委会工作组群1个，准业主群5个，共6个群；接龙群为交房时老邱哥所建，已存在5、6年。
-- **物业立场**：物业方称事先未接到任何沟通，业主群内发接龙属有组织行为，议题未知、未参与。
-- **程序争议**：物业方称欠费人员不能成为业主代表，顶名也不能；业主方称业委会成立之日即自动解除物业合同关系，物业方反驳称起诉期间无法更换物业公司。
-- **表决倾向**：业主代表发言称会议最终结论以表决为主，议题包括小区问题整改、物业去留，原物业也可投标或招标。
-- **调解建议**：办事处代表建议物业拿出真实行动赢得业主信任，双方互相理解，避免矛盾加深。
-## 小区问题清单与物业回应
-- **门柱灯**：业主称入户庭院门柱灯从未开启；物业称因园区能耗成本过高无法运营，业委会曾承诺协助收费后修复。
-- **水系问题**：业主称内部水系、售楼处迎宾水系从未开启；物业称水系从交付起存在严重质量问题，泵无法运转，属地产维修责任。
-- **监控损坏**：业主称监控几乎全部损坏，上个月小区进贼，110派出所及刑警大队未从监控获得数据；物业称已第一时间将拍摄画面截取给派出所和刑警，并出示刑警调取监控照片记录。
-- **监控室服务**：业主称监控室原应24小时有人值班，门铃一键直达功能自王艳芳上任后荒废；物业未正面回应。
-- **绿化维护**：业主称去年大量树木死亡，小区门口光已知就死3棵，物业管家称经理让等明年看能否发芽；物业称业委会10月成立备案，此后为冬季，换树责任归属存疑。
-- **北边围墙**：业主称围墙用烂铁皮遮挡，最西边有缺口，社会人员可随意进出，物业拆除后未安装新围挡，且哄骗业主已定制；物业称该处属红线以外、涉及违建官司，物业有权不处理，曾协调厂家定做但因费用过高未成，已与业委会沟通不下5次。
-- **民生配套**：业主称快递柜、直饮水机、宽带覆盖、暖气开通开户等多年无进展，由业委会全程办理；物业称按建设条例属地产前期配套，后期开通费用由业主承担。
-- **雨水倒灌**：业主称2019年起每逢大雨每家每户有不同程度财产损失，多次反映无进展；物业称园区地势四周高中间矮，车库设计为斜坡向下，属地产前期设计建设问题，超出物业解决范围。
-- **人员配备**：业主称物业办公室从近10人减至4人，维修人员从5人减至2人，配备严重不足；物业称因地产补亏款未结账，现项目20来人，年成本100多万。
-## 物业费欠费与经营状况
-- **欠费金额**：物业方称业主欠物业费170多万，回款40万即可修复部分问题。
-- **收支情况**：物业方称园区年收入100余万，光人工成本100余万，不含垃圾清运费、能耗、维修、税费及办公成本，每年亏损，账目可公开查证。
-- **欠费与服务先后**：业主方认为物业服务无滞后性，不能先收钱再服务；物业方称业委会成员在业主群煽动不缴费，已掌握记录，将走法律程序。
-- **地产公司状况**：物业方称地产公司已申请破产，无法追讨配套费用；办事处代表质疑物业应找地产公司解决，物业称已沟通不下五六遍甚至十遍。
-- **物业费标准**：办事处代表提及售楼合同规定物业费2块5一平方，签订时无业委会。
+## 业主大会召开与表决
+- **业主接龙**：小区业主自发组织接龙，约200名业主支持召开业主大会，主要议题为讨论小区问题及物业去留。
+- **群组结构**：业委会工作组仅1个群，准业主分5个群，共6个群；筹备组6人各联系一部分业主。
+- **接龙群来源**：接龙群为交房时即建立的业主自发群，已存在5、6年，群主为老邱哥。
+- **业主方主张**：业委会或业主个人无权决定撤换物业，须通过业主大会由全体业主表决；建议尽快召开业主大会。
+- **物业方程序质疑**：物业方称召开业主大会前须事先与物业公司沟通，但未接到任何通知，对议题内容不知情、未参与。
+- **物业方诉讼声明**：物业方称已与集团法务沟通，本月将正式起诉业委会，起诉期间业主可能无法行使表决权。
+- **欠费业主资格**：物业方称欠费人员不能成为业主代表，顶名者也不能，将依法追究责任。
+- **业主方决定**：业主方表示将正常推进业主大会，不受物业方起诉影响；物业方称诉讼期间无法更换物业公司。
+## 小区服务问题清单
+- **入户门柱灯**：每家每户入户庭院门柱灯自交房以来从未开启过，业主认为属应得服务未兑现。
+- **内部水系**：业主加价购买水系旁房产，但内部水系自卖房后从未开启过一次。
+- **迎宾水系**：售楼处门口迎宾水系从未开启，业主认为系小区门面，水亦象征财。
+- **监控损坏**：监控几乎全部损坏，上个月小区进贼，110派出所及刑警大队均未从监控获得任何数据。
+- **监控室值班**：交房时配备监控室24小时值班，门铃有一键直达功能，可紧急处理；王艳芳上任后此服务荒废，监控室无人值班。
+- **绿化维护**：绿化维护严重不足，去年死树多棵，小区进门两侧已知死树3棵；业主报修门口病树，物业管家称经理回复等明年看能否发芽长叶。
+- **北边围墙**：小区围墙围上后，北边一直用烂铁皮遮挡，最西边有缺口，社会人员可随意进出；业委会责令整改后物业拆除铁皮，但未再安装，曾称已定制围挡，业主证实并无定制。
+- **民生配套**：快递柜、直饮水机、宽带覆盖、暖气开通开户等民生问题多年无进展，业主多次询问无果，最终由业委会全程办理。
+- **雨水倒灌**：自2019年起每逢大雨雨水倒灌，业主均有不同程度财产损失，多次向物业反映要求完整解决方案，至今无进展。
+- **人员配备**：物业办公室最初近10人，现含经理仅4人；维修人员从5人减至2人；门卫、保洁等人员配备严重不足。
+## 物业方逐条回应
+- **门柱灯**：灯未亮系园区能耗成本过高、物业公司无法运营所致；物业曾与业委会沟通，业委会承诺支持全员缴费并协助收费，收上费用后拿出一部分修复。
+- **水系问题**：水系自交付起存在严重质量问题，所有泵无法正常运转，属地产配套未完成，由地产维修，不属于物业责任。
+- **监控维修**：监控损坏因无费用、超出运营承担；物业公司年保护收入100来万，20多人人工成本100多万，不含垃圾清运费、能耗、维修、税费及办公成本，每年亏损，可公开查账。
+- **监控画面**：警察进入园区时，物业第一时间将拍摄画面截取给派出所和刑警，有刑警调取监控的照片和记录；对业委会所称未拍到监控的信息来源提出质疑。
+- **绿化死亡**：业委会成立于今年10月，备案亦在10月，此后为冬季，非更换绿化季节，更换后死亡责任无法承担。
+- **北边围墙**：北边围墙在物业服务范围红线以外，且涉及法律官司、本身属违建，物业有权不处理；物业曾协调施工单位定做，因费用太高未成，费用本应由物业承担，已与业委会沟通不下5次。
+- **民生配套**：宽带、快递柜、燃气等属地产前期配套，按建设条例和前期配套要求应由地产负责；后期开通物业可协助，费用由业主承担。
+- **雨水倒灌**：园区地势四周高中间矮，车库设计为向内斜坡向下，属地产前期设计和建设是否符合规范的问题，超出物业解决范围。
+- **人员配备**：前期人员充足系地产给了一批补亏款，该款至今未结账；现项目20来人，年成本100多万，今年维修费已花几十万。
+## 物业费与资金问题
+- **欠费金额**：物业方称业主欠物业费170多万，回款40万即可解决部分问题，但账上一分钱没有。
+- **经营亏损**：物业方称年保护收入100来万，人工成本100多万，每年亏损，今年亏损额度拉大；地产公司已申请破产。
+- **业委会引导拒缴**：物业方称业委会成员当面承诺协助缴费，背后却在业主群告知大家不要缴费，相关记录已留存，将走法律程序，以阻碍经营、造成经济损失为由起诉。
+- **业主方观点**：物业服务没有滞后性，全滨州小区没有先收钱再服务的先例；问题系交房以来时序性存在，非物业方来后才出现。
+- **业主方反诉意向**：业主方提出在最终解决前，可能集体起诉要求返还自交房以来未达标服务对应的部分物业费。
+- **恶性循环**：发言者3指出，服务不整改业主不愿缴费，不缴费物业没钱、服务更差，形成恶性循环，区领导、市领导来也难解决。
+## 法律诉讼与反诉
+- **物业方起诉决定**：物业方称已掌握业主群内证据和依据，上午9:52与高级人民法院通话，并与滨城区人民法院沟通，本月正式起诉业委会，包括保洁业主代表。
+- **起诉理由**：物业方称业委会从选举即存在违法行为，后期决策及在业主群煽动均不符职责，另有撬门行为；以阻碍正常经营、造成经济损失为由起诉。
+- **业主方反诉**：业主方称物业窥探业主隐私，只要物业起诉即反诉并拿出证据。
+- **诉讼影响**：物业方称起诉过程可能影响业委会成员个人经营；案件存续期间无法更换物业公司。
+- **业委会合同主张**：业主方称业委会成立之日即自动解除与物业的合同关系。
+## 现场争执与调解
+- **物业经理言论争议**：业主方称进贼时联系物业经理，对方第一句即问「你交物业费了吗？没交物业费不给你服务」，并称「不交物业费上你家吃饭去」；物业方要求拿出录音，业主方称物业经理已承认「上你家吃饭」。
+- **调解建议**：发言者3建议物业拿出真实行动赢得业主信任，双方互相体谅，避免矛盾激化；物业方称已多次明确表态，业主欠费100多万，要求回款40万即修部分问题。
+- **物业方态度**：物业方称公司现状运营困难，不止一次与业委会沟通并留存录像；发言者7称「心里不想去了」，但强调群内信息均已知晓。
+- **业主方态度**：发言者4称已无调解必要，物业不承认遗留问题、不会解决，基本决议为换掉物业；发言者5称99%业主支持其个人看法。
+- **会议结果**：发言者2称今天结果不理想，矛盾隔阂越来越深，未解决实质性问题；发言者3建议办事处再努力协调，双方都是为了工作，没必要把个人牵扯进来。
 ## 结论与决定
-- **物业方决定**：本月正式起诉业委会，已与集团法务沟通，上午9:52与高级人民法院通话，并与滨城区人民法院沟通；起诉理由包括选举违法、决策违规、煽动业主、阻碍经营造成经济损失。
-- **业主方决定**：正常推进业主大会召开，表决物业去留；业主代表称只要业主同意换物业，物业可起诉，双方各自走流程。
-- **物业费返还提议**：业主代表提出在最终解决前，可能集体起诉要求返还交房以来未达成服务的物业费部分。
+- **业主方决定**：正常推进业主大会，由全体业主表决物业去留；业主方表示物业可起诉，业主方按自身流程推进。
+- **物业方决定**：本月正式起诉业委会，以阻碍正常经营、造成经济损失为由；已与集团法务及高级人民法院、滨城区人民法院沟通。
+- **未达成一致**：双方就业主大会能否在诉讼期间召开、物业费欠费与服务质量责任归属、物业合同是否自动解除等问题未达成一致。
+## 行动项与分工
+- **物业方**：本月内完成起诉手续，集团法务今日操作相关手续。
+- **业主方**：正常推进业主大会召开流程。
+- **物业方**：可公开查账，供业主核实经营收支情况。
 ## 待确认与风险
-- **诉讼期间业主大会能否召开**：物业方称案件存续期间无法更换物业公司，业主方认为若无法律明文禁止则应照常召开，双方未达成一致。
-- **物业经理言论争议**：业主称物业经理曾说不交物业费就上门吃饭，物业方否认并要求提供录音，双方各执一词。
-- **欠费与服务改善先后**：物业称先回款40万再修复，业主称服务达标才缴费，循环争论未解。
-- **安全隐患**：北边围墙缺口未封闭，社会人员可随意进出；上个月进贼未获监控数据；雨水倒灌问题未解决，明年大雨可能再淹。
-- **物业经营风险**：物业方称每年亏损，地产公司已申请破产，欠费170多万，服务改善缺乏资金支撑。</t>
+- **业主大会召开受阻风险**：物业方起诉可能导致诉讼期间业主大会无法召开，双方对此存在分歧。
+- **欠费与服务恶性循环**：业主欠费170多万，物业无资金维修，服务不改善则业主更不愿缴费，矛盾持续加深。
+- **治安风险**：北边围墙缺口未封闭、监控几乎全部损坏，社会人员可随意进出小区，上月已发生进贼事件。
+- **雨水倒灌风险**：问题自2019年未解决，明年大雨可能再次造成业主财产损失。
+- **隐私争议**：业主方质疑物业窥探业主隐私，物业方称已截屏留存业主群动态作为证据，双方将进入诉讼程序。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>67.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/4468</t>
+          <t>21511/5566</t>
         </is>
       </c>
     </row>
@@ -2406,89 +2415,84 @@
       <c r="C6" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌论坛以「具身智能技术路线与产业前景」为主题，由主持人发言者2组织，汇聚了来自学术界的多位教师（发言者3、5、6、7、9、11）、业界嘉宾（发言者10）及博士生（发言者4、8），围绕具身智能领域的关键技术路线、学术分歧与产业落地前景展开深入研讨。论坛旨在通过学术与产业视角的碰撞，厘清具身智能在模型架构、策略学习、数据获取等核心问题上的现状与未来方向。
-- **具身智能的形态与硬件期待**：探讨具身智能最终会收敛为何种形态（人形机器人或特种机器人），以及现有硬件（如工业机械臂）在寿命、可靠性、柔顺性等方面能否支撑大规模真机评估与软硬件协同优化。
-- **世界模型的定义与分歧**：核心争议在于强化学习领域与计算机视觉领域对世界模型的理解差异，包括其是否必须可交互、是否需要三维表征（3D/物理规律），以及世界模型能否统一为一个通用模型。
-- **强化学习与模仿学习的路线之争**：讨论在数据有限、仿真环境不完美的现实约束下，未来策略学习的最终路线是纯模仿学习、纯强化学习，还是「先模仿后强化」或「模型强化加机理融合」等混合方案。
-- **数据采集与仿真数据的作用**：聚焦如何获取高质量的真机数据（如视角控制、标定、物体运动信息），以及仿真数据与真实数据的配比、仿真数据能否弥补真机数据不足、互联网视频数据是否可用等问题。
-- **国产仿真系统的产业问题**：探讨中国具身智能仿真是否将强依赖英伟达生态，以及是否存在国产替代方案以应对潜在的「卡脖子」风险。
+本次圆桌论坛由发言者2主持，围绕具身智能领域的关键技术问题展开，多位嘉宾与博士生参与讨论。发言者2代表多模态大模型与具身智能融合方向，并介绍雄辉（于洋老师博士生，强化学习方向）、薛寒（卢策武老师博士生，数据收集与柔性物体操作方向）、志龙（于洋老师博士生，具身模型与世界模型方向）等博士生参与。研讨旨在探讨具身智能的大模型架构、硬件形态、世界模型定义、策略学习路线及数据采集等核心议题，各方观点碰撞，未形成统一结论。
+- **具身智能大模型架构**：讨论端到端模型与分层模型（如固定前段加Action refiner）的优劣，以及大模型是否应从感知到控制全链路统一。
+- **具身智能硬件形态**：探讨具身智能的物理载体最终收敛为人形机器人还是特种机器人形态，以及硬件对算法发展的支撑与期待。
+- **世界模型的定义与实现路径**：讨论强化学习领域与计算机视觉领域对世界模型的不同理解，以及是否需要三维归纳偏置、是否应统一模型。
+- **强化学习与模仿学习的路线之争**：探讨未来策略学习最终路线是强化学习、模仿学习还是两者混合，以及各自在数据、仿真、落地方面的瓶颈。
+- **数据采集与仿真数据**：讨论真机数据与仿真数据的成本、质量与规模化路径，以及互联网视频数据、可穿戴设备、无标注数据等新数据来源的可行性。
+- **国产仿真系统**：探讨中国具身智能仿真是否强依赖英伟达生态，以及国产替代产品的可能性。
 # 核心观点
-## 具身形态与硬件期待
-- **发言者3（机械与传感器方向）**：提出具身智能最终形态问题——是像人一样的人形机器人，还是像《星际穿越》中可变形的大方块；机械领域有「机械智能」概念，软手可通过强摩擦与顺应性在较大误差下仍抓得牢，询问算法与软件视角对硬件学科的期待。
-- **发言者4（博士生）**：硬件需要高寿命与高可靠性；训练VLA并在真机大规模评估时，模型预测撞桌等失误会导致机器人损坏，难以可靠scale up；现有工业机械臂并非为此设计，需要个人柔顺的硬件结构以支持规模化真机评估。
-- **发言者2（主持人）**：具身智能是软硬件协同优化的范式；以松灵两代产品为例，第二代在遥操与策略部署上明显优于第一代；与任老师合作的凝胶夹爪可反馈触觉、增加摩擦力、抓取更稳。
-- **发言者5（嘉宾）**：若大模型从上到下贯通，会消除硬件迭代的可能性——新硬件（如软体机器人）出现时大模型需完全重新训练；模型至少应分两层，大脑不变、小脑adaptive到肢体；以手断后大脑仍能指挥右手泡咖啡为例，底层控制模型（小脑）需随肢体惯量变化而调整。
-- **发言者6（嘉宾）**：从第一性原理出发，现实中的桌椅等均为人设计，人形机器人（双足或轮式、带灵巧手）会占很大比例；特种机器人（如车厂、微电子制造厂中实现97%以上自动化的各类机械臂）也大量存在，两类将并存。
-## 世界模型的定义与分歧
-- **发言者8（博士生，强化学习方向）**：强化学习领域世界模型的第一要义是**可交互**——概念可回溯至1990年Sutton的Dyna-Q文章，定义为黑盒、输出下一时刻观测；2018年Schmidhuber与LeCun定义的世界模型含表征与转移两个组件；当前世界模型在物理规律体现上欠缺明显，希望引入3D、触觉等多模态信息完善。
-- **发言者7（嘉宾，CV方向）**：CV界发展多年就是为了动态重建物理世界，可作为RL世界模型的工具，但目前仍不成熟；三维CV技术栈深，RL博士生难以完全学习，导致RL界不太关注三维表征；RL与CV对world models的关注点不同——一个更端到端、一个更关注解耦表征。
-- **发言者7（嘉宾）**：提出**数据规模与inductive bias的权衡**——数据足够多时需要的inductive bias变少，数据少时需要的更多；以ImageNet、GPT的成功说明大规模学习可替代inductive bias，而Uni3D等新模型又需要3D inductive bias；学术发展呈螺旋前进，world models是否需要3D inductive bias最终由数据决定。
-- **发言者5（嘉宾）**：世界模型可能**无法统一**——以游戏主角跳楼为例，游戏与物理世界观测完全一致但结局不同，一个世界模型同时acquire两个dynamics存在歧义问题；policy有可能统一（同一大脑可同时玩游戏中跳楼与在现实中避免跳楼），但world model大概率做不到，应为多个。
-- **发言者9（嘉宾）**：提出反对意见——强化学习的世界模型是**任务导向**的，目标是更好地学策略，只需产出latent state或reward即可；CV世界模型做得足够好可用于强化，但为解强化任务是否需要CV式世界模型「总觉得不必要」。
-- **发言者5与发言者9交锋**：发言者9提出不同物理结构可有相同统一表征、仍算统一模型；发言者5回应称这等于在模型中加入condition（区分游戏或真实），但M个独立世界模型比一个高维可控condition的世界模型更简单可实现，且目前没有atari game能靠一个world model建模所有游戏。
+## 硬件形态与模型收敛
+- **发言者3（机械领域视角）**：提出具身智能硬件形态的收敛问题——是像人一样的人形机器人，还是像科幻片中可变形的大方块；机械领域存在「机械智能」思路，如软手通过强摩擦和顺应性，在抓取误差较大时仍能抓牢。
+- **发言者4（博士生）**：硬件需高寿命与高可靠性；具身智能训练中模型预测失误易导致机器人撞桌损坏，现有工业机械臂并非为此设计，需要个人柔顺的硬件结构以支持大规模真机评估的scale up。
+- **发言者2（主持人）**：具身智能是软硬件协同优化的范式；以松灵两代产品为例，第二代在遥操与策略部署上明显优于第一代；与任老师合作的凝胶夹爪可反馈触觉、增加摩擦力，体现协同进化。
+- **发言者5（嘉宾）**：若大模型从上到下直通，会消除硬件迭代的可能性——新硬件（如软体机器人）出现时大模型需完全重新训练；模型至少应分大脑与小脑两层，大脑不变、小脑adaptive到肢体（以手断后大脑仍能指挥右手泡咖啡为例）。
+- **发言者6（嘉宾）**：从第一性原理出发，人形机器人因现实环境（桌椅等）为人而设计必然存在，可能是双足或轮式并配灵巧手（引马斯克采访：公司花一半精力做22自由度灵巧手）；特种机器人在工业制造中已大量存在（车厂、微电子制造厂机械臂实现97%以上自动化），两类将并存。
+- **发言者7（嘉宾）**：从产业角度预测具身智能融资将经历四波——第一波后过完年进入低谷，第二波接近自动驾驶融资规模，第三波接近大模型规模，第四波接近互联网规模；每波技术变革将深刻改变具身大模型硬件与云端模型形态，时间取决于技术突破。
+## 世界模型的定义与实现路径
+- **发言者8（博士生，强化学习视角）**：世界模型概念可回溯至1990年强化学习之父Sutton的Dyna-Q文章，本质是黑盒、输出下一时刻观测，第一要义是**可交互**（最终目的是学策略）；2018年Schmidhuber与杨立昆定义的世界模型含表征与转移两个组件；当前世界模型在物理规律体现上欠缺明显，希望引入3D、触觉等多模态信息完善。
+- **发言者7（嘉宾，CV视角）**：CV界共识是计算机视觉发展多年就是为了动态重建物理世界，可作为RL世界模型的被调用工具；但三维CV技术栈深，RL博士生难以完全学习，导致RL领域不太关注三维表征——这是学术发展阶段导致的现状。
+- **发言者7（嘉宾）**：提出数据规模与归纳偏置（inductive bias）的权衡——数据足够多时需要的归纳偏置变少，数据少时需要的更多；以ImageNet、GPT的成功说明大规模学习可不需要归纳偏置，以UniSim说明当前仍需3D归纳偏置；学术发展呈螺旋前进，世界模型是否需要3D归纳偏置最终由数据决定。
+- **发言者5（嘉宾）**：以游戏主角跳楼与真人cosplay为例——两者观测完全相同但结局不同（游戏稳落地、现实死亡），世界模型无法同时acquire两个dynamics，因这是完全歧义的问题；**世界模型可能无法统一（应是多个），但policy有可能统一**，因为人作为同一policy既能玩游戏也能在现实中避免跳楼。
+- **发言者9（嘉宾）**：提出反对意见——强化学习的世界模型是任务导向的，目标只是更好学策略（产生latent state或reward即可），CV世界模型做得足够好可用于强化，但为解强化任务未必需要；针对发言者5的歧义问题，提出不同物理结构可有相同统一表征、policy能识别condition则world model也能识别的反例。
+- **发言者5（嘉宾）回应**：加condition后问题变成复杂度权衡——M个独立世界模型 vs 一个高维可控condition的世界模型，从可实现角度M个模型更简单；目前没有atari game能靠一个world model建模所有游戏；policy可通过更长的observation窗口隐式体现condition，但用GPT模型回归atari games大概率是强记。
 ## 强化学习与模仿学习的路线之争
-- **发言者10（业界嘉宾）**：公司采用**模型强化加机理融合**方式；监督学习在具身任务中动作空间大、数据分布远不足以覆盖高维动作；纯强化学习强依赖仿真环境，sim-to-real迁移困难；实物强化学习需严格限定决策规模与任务设定，直接学到从观测到电流的控制非常困难；其强化PC工作采用任务分层——上层强化学习做决策，底层用MPC、DWA等传统方法执行，整体性能有提升。
-- **发言者9（嘉宾）**：同意混合路线，不认为强化或模仿能单独收敛到最终解；底层PID等传统方法已能解决的场景没必要从零替代；复杂问题历史规律都是**先模仿后强化**（如AlphaStar、GPT）——from scratch跑强化样本复杂度不可接受，模仿提供好的先验信息；单独模仿无法达到专家水平（除非任务就是模仿专家），单独强化也不行（除非任务足够简单）。
-- **发言者5（嘉宾）**：PID能做的系统必然有反馈，反馈可直接作为强化学习执行过程中的reward；过去用PID效果不够好，现在通过强化可做得更好。
-- **发言者11（嘉宾）**：模仿学习与强化学习**并不冲突**——学人类运动先验可用DeepMind的模仿学习，也可用强化学习优化；有现成数据就从模仿学习角度做，没有数据（如复杂人类运动）就先用强化学习获取，再以BC形式建模latent；有了latent后可用RL快速找到对应状态完成任务。
-## 数据采集与仿真数据的作用
-- **发言者11（嘉宾）**：数据质量关键在于**视角控制与标定**——Open X等数据集融合多家数据、相机视角无法固定，而视角非常影响policy表现；手眼标定至今仍有人在发文章、解决得不好；Open X等数据集只捕捉本体信息（末端、关节角度、力矩），缺少物体运动信息；其采集方案记录刚体和关节体的物理变化过程。
-- **发言者4（博士生）**：all in **reward采集路线**；柔性体操作（叠衣服、系鞋带、拉拉链）现有仿真需IPC等先进图形学技术，算力要求高且掌握者少（如UCLA蒋正凡夫），进展慢；reward采集是相对低成本方案——「现实生活就是最好的仿真器」。
-- **发言者4（博士生）**：终极采集形态可能是脑机接口或机电方式，无感采集多模态数据；现阶段可穿戴式设备在人们做事过程中采集是较能scale的方案；互联网视频数据与机器人所需数据差异大——网上叠衣服视频都是平铺状态教学，但机器人见到的是从洗衣机取出揉成一团的状态，没人会拍视频教这些「人类从小就会」的事。
-- **发言者2（主持人）**：互联网数据质量低——本人受ego4d数据集「毒害」，清洗耗时三个月；数据金字塔中互联网数据在最底层；仿真数据分传统仿真（如周扣）与强化训练policy收集的数据；其团队实验显示**300条仿真数据加20条真机数据即可显著提升成功率**，方法仅为pretrain后真机数据微调几次。
-- **发言者7（嘉宾）**：真实数据还是仿真数据应**case by case看成本**——室内服务机器人真机数据收集有可行性，但自动驾驶corner case（如鬼探头）让人去采集太危险；应加入第三个domain——**无标注真实数据**，如Segment Anything、Depth Anything；2025年主题应是「在自动驾驶和具身智能领域推广大规模利用无标注数据」，不要再讨论1:9、2:8、5:5这类有标注数据配比。
-## 国产仿真系统的产业问题
-- **发言者2（主持人）**：询问未来中国是否强依赖英伟达生态（Isaac Sim/Isaac Lab已开放柔性物体仿真接口），还是可以有国产产品支持仿真。
-- **发言者7（嘉宾）**：宋应等公司赌「以后会被卡脖子」，在做国产替代，生意本身很好；但产业问题复杂——有人在做这个生意，技术上最终会比较统一，business上很复杂，因为赌的是脱钩与卡脖子。
+- **发言者10（业界嘉宾）**：公司采用模型强化加机理融合方式；监督学习在具身任务中动作空间大、数据分布远不足以支撑高维动作，强化学习强依赖仿真环境、纯RL路线难以做到sim-to-real迁移；需将RL的决策空间与任务设定（state-action对）做很好限定，如上层RL做决策、底层用MPC或DWA等传统方法执行，实际部署中能提升整体性能。
+- **发言者9（嘉宾）**：同意混合方式，不认为收敛到最后强化或模仿能单独完成；复杂问题历史规律都是先模仿后强化（如AlphaStar、GPT）——from scratch跑强化样本复杂度不可接受，人类模仿提供的先验信息没有坏处；单独模仿不行（人类行为不一定最优解，需强化达到superhuman），单独强化也不行（除非任务足够简单）。
+- **发言者5（嘉宾）**：PID控制必有反馈（无反馈做不了控制），因此凡PID能做的系统必然有反馈，可完全拿该反馈作为强化学习执行过程中的reward；过去用PID效果不够好，现在通过强化做得更好。
+- **发言者11（嘉宾）**：模仿学习与强化学习并不冲突——学人类运动先验可用基于强化学习的DeepMind Motion Matching，也可用模仿学习；有现成数据就从模仿学习角度做，没有数据（如复杂运动）就先用RL获取再以BC形式建模latent；有了latent后完成任务可通过RL快速找到对应latent。
+## 数据采集与仿真数据
+- **发言者11（嘉宾）**：数据质量关键在于视角控制与标定——Open X等数据集融合多家数据、相机视角无法固定，而视角非常影响policy表现；手眼标定看似已解决但至今仍有人在发文章、解决得不好；Open X等数据集只捕捉本体信息（末端、关节角度、力矩），缺少物体运动，OpenLink从采集出发必须记录物体运动（当时设备有限只能采集刚体和关节体）。
+- **发言者4（博士生）**：all in真实数据采集路线；柔性体操作（叠衣服、系鞋带、拉拉链）现有仿真需IPC等先进图形学技术、算力要求高且掌握者少（如UCLA蒋正凡夫），进展缓慢；真实数据是相对低成本方案——「真实世界本身就是最好的仿真器」。
+- **发言者4（博士生）**：现有采集方式难以scale——派林收集1万小时数据，即使融资再多一两个数量级也达不到GPT-2、GPT-3级别；终极形态可能是脑机接口或机电方式无感采集多模态数据，现阶段可通过可穿戴设备在人们日常做事时采集；互联网视频数据与机器人所需数据差异大——网上教叠衣服的视频都是平铺状态，但机器人见到的是从洗衣机拿出揉成一团的状态，人类习以为常的简单事恰恰是机器人最缺的数据。
+- **发言者2（主持人）**：互联网数据在数据金字塔最底层、质量低——本人受ego4d数据集「毒害」，清洗耗时三个月；仿真数据可弥补真实数据不足——300条仿真数据训出的策略直接去真实世界成功率很低，但300条仿真数据加20条真机数据成功率显著提升（用很原始的fine-tune方法）；仿真数据可包含物体随机位置、随机orientation、任意初始状态。
+- **发言者7（嘉宾）**：真实数据还是仿真数据应case by case看成本——室内服务机器人真机数据收集有可行性，但自动驾驶corner case让人去「鬼探头」太危险；**提出2025年应迈向大规模利用无标注真实数据**（如segment anything、depth anything），不再讨论真实与仿真有标注数据的比例问题（1:9、2:8、5:5等观点已过时）。
+- **发言者7（嘉宾）**：国产仿真系统是产业问题——宋应等团队赌会被卡脖子、做国产替代，business by business是很好的生意；技术上最终会比较统一，但business上很复杂，取决于是否脱钩卡脖子。
 # 达成共识与解决方案
-## 达成共识与解决方案
-**未形成统一结论**。本场讨论围绕具身智能的形态、世界模型、策略学习路线与数据采集等议题展开，各方观点存在明显分歧，未达成一致结论。但讨论中形成了若干倾向性认识与主流意见，具体如下：
-### 具身形态与硬件
-- **软硬件协同优化是共识**：发言者2提出具身智能一定是软硬件协同优化的范式，并以松灵产品两代迭代为例——第二代在遥操与策略部署上明显优于第一代；夹爪加凝胶后可反馈触觉且抓取更稳、摩擦力更好。发言者5从模型分层角度呼应，认为硬件变化不应要求大脑模型重训，而应由小脑层适应新肢体动力学。
-- **硬件需为大规模真机评估设计**：发言者4指出现有工业机械臂并非为大规模真机评估设计，模型预测失误导致的碰撞会损坏设备，阻碍可靠扩展；需要个人柔顺的硬件结构支持规模化真机评估。
-- **人形与特种机器人将并存**：发言者6认为从第一性原理出发，现实环境（桌椅等）为人而设计，人形机器人（双足或轮式、带灵巧手）会占很大比例；同时特种机器人（如车厂、微电子制造厂中已实现97%以上自动化的各类机械臂）也将大量存在。
-### 世界模型
-- **CV与RL两界关注点不同是现状**：发言者7指出，CV界追求动态重建物理世界，可作为RL中世界模型的工具，但三维计算机视觉技术栈深，RL博士生难以完整学习，导致RL界不太关注三维表征；发言者8从强化学习角度确认，RL领域世界模型的第一要义是可交互（源自1990年Dyna-Q），其次是物理规律，最后才是引入3D等多模态信息。
-- **数据规模决定inductive bias需求**：发言者7提出，大规模机器学习中数据足够多时需要的inductive bias会变少，数据少时需要的更多；当前在NeurIPS上刷高分为需要3D inductive bias，但未来数据规模化后更端到端的方式会更好，学术发展呈螺旋前进状态。
-- **世界模型是否统一存在根本分歧**：发言者5认为世界模型可能无法统一——同一观测（如从楼上跳下）在游戏与物理世界会有不同结局，是歧义问题，一个世界模型难以同时建模两个dynamics；发言者9提出反例，认为可通过在模型中加condition（区分游戏或真实）实现统一，但发言者5回应称M个独立模型比一个高维可控condition模型更简单可实现，且目前没有能建模所有Atari游戏的世界模型。
-### 策略学习路线
-- **当前阶段宜采用混合方案**：发言者10从产业部署经验出发，认为监督学习数据分布远不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且sim-to-real迁移困难，故公司采用模型强化加机理融合方式；发言者9表示同意，认为复杂任务应先模仿后强化，单独模仿无法超越专家水平，单独强化样本复杂度不可接受。
-- **底层可复用传统方法**：发言者10指出，强化学习决策空间与任务设定需良好限定，上层做决策、底层用MPC或DWA等传统方法执行，即可提升整体性能；发言者9补充，PID等传统方法已能解决很多场景，没必要从零替代。
-- **模仿与强化并非本质冲突**：发言者11认为两者只是获取运动先验的不同方式——有现成数据可用模仿学习，没有数据（如复杂人体运动）可用强化学习生成，再建模latent完成后续任务。
-- **PID可解系统必有反馈可作reward**：发言者5回应真机reward获取问题，认为PID能做的系统必然包含反馈，该反馈可直接作为强化学习执行过程中的reward。
-### 数据采集与仿真
-- **数据质量关键在于视角与标定**：发言者11指出Open X等数据集相机视角无法固定、影响策略表现，其团队采集时严格控制视角与标定，并记录物体运动（刚体与关节体）而不仅是本体信息。
-- **仿真数据与真机数据结合有效**：发言者2报告实验结果，300条仿真数据训出的策略直接真机测试成功率很低，但加上20条真机数据后成功率显著提升，所用方法仅为预训练后真机数据微调。
-- **互联网视频数据与机器人所需数据差异大**：发言者4举例，网上叠衣服视频展示的是平铺状态，而机器人需处理从洗衣机取出揉成一团的状态，此类常见场景无人拍摄教学视频，恰是机器人最缺的数据。
-- **无标注真实数据应成为新方向**：发言者7提出2025年应迈向同时使用真实与仿真的有标注数据，并大规模利用无标注真实数据（如segment anything、depth anything），不再纠结真实与仿真数据的比例问题。
-- **可穿戴设备是规模化采集的可行路径**：发言者4认为终极形态是脑机接口或机电方式实现无感多模态采集，现阶段可穿戴设备在人们日常活动中采集数据是较能scale的方案；发言者2补充，可穿戴设备精度相比遥操数据仍需覆盖GAP。
-### 国产仿真系统
-- **国产替代需求存在但产业问题复杂**：发言者2提出中国是否强依赖英伟达生态的问题；发言者7回应称有公司（如宋应）赌卡脖子风险、做国产替代，但产业问题复杂，涉及脱钩与标准化等多重因素，技术最终会统一，business层面则更复杂。
+**未形成统一结论**。本场研讨围绕具身智能的硬件形态、世界模型、策略学习路线与数据来源四个议题展开，各方观点存在明显分歧，未达成一致意见。但讨论中形成了若干倾向性认识与主流意见，具体如下：
+## 硬件形态与模型架构
+- **软硬件协同优化**：发言者2提出具身智能是软硬件协同优化的范式，以松灵产品两代迭代为例，第二代在遥操与策略部署上优于第一代；夹爪加凝胶后可反馈触觉、增加摩擦力，说明硬件改进能提升算法性能。
+- **模型分层而非统一**：发言者5主张大模型不应从上到下完全统一，至少应分大脑与小脑两层——大脑保持稳定，小脑需适应肢体变化（以手断后大脑仍能工作、小脑需适应新构型为例）；发言者6认为当前多模态大模型微调方案不是终极形态，世界模型可能更接近人脑水平，但人形与特种机器人将并存。
+- **硬件可靠性要求**：发言者4提出具身智能实验用硬件需高寿命、高可靠性，现有工业机械臂易因模型预测失误撞坏，难以支撑大规模真机评估，需个人柔顺硬件结构支持scale up。
+## 世界模型
+- **两领域定义差异**：发言者8指出强化学习领域世界模型概念源于1990年Dyna-Q，核心是可交互性（输入观测与动作、输出下一时刻观测）；发言者7认为CV界世界模型追求动态重建物理世界，可作为RL世界模型的工具，但当前技术不成熟，且RL与CV关注点不同——RL更端到端，CV更关注解耦表征。
+- **数据规模与归纳偏置权衡**：发言者7提出数据规模与归纳偏置存在权衡——数据充足时归纳偏置需求减少，数据稀缺时需要更多归纳偏置；以ImageNet、GPT成功说明大规模学习可减少归纳偏置，而UniSim等新模型仍需三维归纳偏置。
+- **世界模型统一性存疑**：发言者5认为世界模型可能无法统一，因存在歧义问题（游戏与物理世界观测相同但动力学不同）；发言者9认为强化学习的世界模型是任务导向的，CV世界模型并非必要，但不同物理结构可共享统一表征。
+## 策略学习路线
+- **混合路线倾向**：发言者10表示公司采用模型强化加机理融合方式，因监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且难以迁移；发言者9认为复杂任务应先模仿后强化，单独模仿无法超越专家水平，单独强化样本复杂度不可接受，但工程手段可解决先模仿后强化可能带来的问题。
+- **反馈作为奖励信号**：发言者5提出PID控制必有反馈，可将其作为强化学习在执行过程中的奖励信号，这是真机强化学习reward获取的可行路径。
+- **模仿与强化不冲突**：发言者11认为两者并非本质冲突，可先通过模仿学习或强化学习获取运动先验（latent），再通过强化学习完成任务。
+## 数据采集与仿真
+- **仿真数据加少量真机数据**：发言者2提出仿真数据可弥补真机数据不足——300条仿真数据训出的策略直接部署真机成功率很低，但加上20条左右真机数据后成功率显著提升；仿真数据可覆盖物体随机位置、朝向与初始状态。
+- **数据质量关键要素**：发言者11强调数据采集时视角控制与标定至关重要（手眼标定至今仍有文章在解决），且必须记录物体运动而不仅是本体信息；发言者2指出互联网数据质量低，ego4d数据集清洗耗时三个月。
+- **真实数据规模化路径**：发言者4认为真实数据是低成本方案（相比高性能仿真算力），但现有采集方式难以达到GPT-3级别数据量；提出终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备是可行方案；互联网视频数据与机器人所需数据差异大（如叠衣服场景，网上视频多为平整状态教学，机器人需处理从洗衣机取出揉成一团的初始状态）。
+- **无标注数据利用**：发言者7提出2025年应大规模利用无标注真实数据（如segment anything、depth anything），不再局限于讨论有标注真实数据与仿真数据的配比。
 # 未决分歧与后续探索
-## 具身形态
-- **人形还是特种机器人**：发言者6认为现实环境（桌椅等）为人而设计，人形机器人（双足或轮式、带灵巧手）会占很大比例，同时车厂、微电子制造厂已有97%以上自动化采用特种机械臂，两类将并存；发言者3提出具身形态是否会收敛为人形或科幻片中可变形形态的疑问，未获一致回应。
-- **大模型是否贯通至硬件层**：发言者5主张大模型不应从上到下贯通，至少应分两层——大脑不变、小脑自适应肢体，并以人手断后大脑仍能工作、底层控制需适应新构型为例；发言者6认为当前多模态大模型微调方案不是终极形态，世界模型可能更接近但也不是最终答案，最终可能需全新网络架构，难以预测。
-## 世界模型
-- **世界模型是否应统一**：发言者5认为世界模型无法统一，因存在歧义问题（同一观测对应不同物理结局，如游戏与现实中跳楼结果不同），而policy可能统一；发言者9提出反例，认为不同物理结构可通过统一表征加condition实现统一模型，发言者5回应称这需将M个独立模型装入高维可控condition模型，工程上更复杂，且现有atari游戏尚无单一世界模型成功案例。
-- **CV与RL世界模型的定位**：发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，但当前仍不成熟，且三维视觉技术栈深，RL博士生难以完全掌握，导致RL领域不太关注三维表征；发言者9认为强化学习的世界模型是任务导向的，只要有助于学策略即可，CV世界模型并非必要。
-- **inductive bias的必要性**：发言者7提出数据规模与inductive bias的权衡假设——数据多时bias需求减少、数据少时需求增加，并称梦想写一篇题为data bias trade off的论文；发言者9对此提出质疑，认为不能简单以是否带inductive bias区分CV与RL世界模型的优劣。
-## 强化学习与模仿学习
-- **最终路线**：发言者10（业界）主张现阶段采用模型强化加机理融合，因监督学习数据分布不足以覆盖高维动作空间，纯强化学习又强依赖仿真环境、sim-to-real迁移困难；发言者9认为复杂任务应先模仿后强化，单独模仿或单独强化均不可行，并称有学术论文宣称先模仿再强化效果不好，但工程手段可解决；发言者11认为两者并不冲突，只是获取运动先验的不同方式——有数据用模仿学习，无数据可用强化学习生成。
-- **真机reward获取**：发言者2提问真机复杂任务中reward如何获取（仿真有上帝视角，真机传感器有偏差）；发言者5回应称PID能做的系统必有反馈，该反馈可直接作为强化学习的reward。
+## 硬件形态与模型架构
+- **具身智能硬件形态收敛方向**：发言者3提出疑问，具身智能身体最终收敛为人形机器人还是科幻片中可变形形态；发言者6认为人形机器人与特种机器人将并存——人形因现实环境为人设计而存在，特种机器人在车厂、微电子制造厂等场景已实现97%以上自动化；发言者7从产业角度预测，未来三至四波技术变革将深刻改变具身大模型的硬件与云端模型形态，具体形态暂时无法预测。
+- **大模型是否应从上到下统一**：发言者5主张不应是单一模型贯通最上至最下，至少应分大脑与小脑两层——以手断后大脑仍能工作、小脑需适应肢体变化为例，认为小脑应adaptive到肢体，而非更换大脑；发言者6认为当前多模态大模型微调方案不是终极方案，世界模型可能更接近人类水平，但人脑新架构出现前难以预测最终形态。
+- **硬件可靠性需求**：发言者4提出具身智能实验需要硬件高寿命与高可靠性，现有工业机械臂并非为大规模真机评估设计，撞几次即损坏，难以可靠scale up，需要个人柔顺的硬件结构支撑规模化评估；发言者2认为具身智能是软硬件协同优化范式，以松灵两代产品对比说明硬件迭代提升遥操与策略部署效果，凝胶夹爪可反馈触觉且抓取更稳。
+## 世界模型定义与实现路径
+- **世界模型是否需要三维归纳偏置**：发言者7认为CV界世界模型追求重建物理世界，可作为RL世界模型的工具，但当前技术不成熟；三维表征技术栈深，RL博士生难以完全学习，导致RL领域不关注三维表征；发言者7提出数据规模与归纳偏置的权衡——数据多时归纳偏置需求减少，数据少时需求更多，并称梦想写一篇题为data bias trade off的论文；发言者8从强化学习角度指出世界模型第一要义是可交互，源于1990年Dyna-Q，当前世界模型在物理规律体现上欠缺明显。
+- **世界模型能否统一**：发言者5认为世界模型可能无法统一——以游戏主角跳楼与物理世界跳楼结局不同为例，相同观测对应不同dynamics，存在完全歧义问题，M个独立世界模型比一个高维可控condition模型更可实现；发言者9提出反例，认为不同物理结构可有相同统一表征，policy能识别condition，世界模型为何不能；发言者5回应称加condition后工程难度高，用GPT模型回归atari games大概率是强记；发言者9认为强化学习的世界模型是任务导向的，CV世界模型并非必要，只要有助于学策略即可。
+## 强化学习与模仿学习路线
+- **最终策略学习路线**：发言者10表示公司采用模型强化加机理融合方式，因监督学习数据分布远不足以覆盖高维动作空间，纯强化学习强依赖仿真环境、sim-to-real迁移困难，需将强化学习决策空间与任务设定限制好，上层用强化学习做决策、底层用MPC或DWA等传统方法执行；发言者9认为复杂任务应先模仿后强化，单独模仿无法达到专家水平（除非任务即专家行为），单独强化样本复杂度不可接受，先模仿再强化不会导致强化效果变差，工程手段可解决；发言者11认为模仿学习与强化学习并无本质冲突，运动先验有数据可用模仿学习获取，无数据可用强化学习生成，再通过强化学习完成任务。
+- **真机强化学习的奖励获取**：发言者2提出真机复杂任务中reward如何获取的问题，仿真中有上帝视角，真机上detection与传感器有偏差；发言者5回应称PID控制必有反馈，所有PID能做的系统必然有反馈，可完全拿该反馈作为强化学习的reward，过去PID效果不够好，现在通过强化可做得更好。
 ## 数据采集与仿真
-- **仿真与真实数据比例**：发言者7称讨论中提及1:9、2:8、5:5等观点，未达成一致，主张2025年应迈向大规模利用无标注真实数据（如segment anything、depth anything），并称这将成为其个人主题；发言者2分享其300条仿真数据加20条真机数据可显著提升成功率的实验结果。
-- **数据采集方式**：发言者4主张reward采集路线，认为现实世界是最好的仿真器，终极形态是脑机接口或机电等无感多模态采集方式，现阶段可穿戴设备是较能scale的方案；发言者2认为可穿戴设备精度相比遥操数据有差距，需与仿真数据配合覆盖GAP。
-- **互联网视频数据可用性**：发言者4指出互联网视频与机器人所需数据差异大——如叠衣服视频多为平整状态教学，缺少洗衣机取出后揉成一团的混乱状态数据，而这类常见任务恰是机器人最缺的数据；发言者2称深受ego4d数据集之害，清洗耗时三个月。
-## 国产仿真系统
-- **是否依赖英伟达生态**：发言者2提问中国未来是否强依赖英伟达生态，或可有国产产品支持仿真；发言者7回应称有公司（如宋应）赌卡脖子风险、做国产替代，产业问题复杂，技术上最终会较统一，但business层面是复杂问题。</t>
+- **真实数据与仿真数据比例**：发言者7认为应case by case看成本，室内服务机器人真机数据收集有可行性，自动驾驶corner case收集危险；发言者7提出2025年应迈向大规模利用无标注真实数据，如segment anything、depth anything，不再讨论真实与仿真有标注数据的比例问题。
+- **数据采集规模化方案**：发言者4主张真实数据是低成本方案，现实生活是最好的仿真器，但现有采集方式即使多一两个数量级也难以达到GPT-2、GPT-3级别数据量，终极形态可能是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备在人们做事过程中采集是较能scale的方案；发言者4指出互联网视频数据与机器人所需数据差异大——网上教叠衣服的视频是平铺状态，机器人需要的是从洗衣机取出揉成一团再展平的数据，常见易完成的事情恰是机器人最缺的数据。
+- **数据质量与视角控制**：发言者11强调采集数据时视角控制与标定非常重要，open X等数据集相机视角无法固定、影响policy表现，且只捕捉本体信息、缺少物体运动，orkin从采集角度出发必须记录物体运动，设备有限时只能采集刚体和关节体。
+- **仿真数据与真机数据结合**：发言者2表示用仿真生成300条数据训完策略直接去真实世界测试成功率很低，但300条仿真数据加20条左右真机数据成功率显著提升，方法只是pretrain一个model再用真机数据微调；发言者2指出柔性物体仿真并非解决不了，而是图形学领域认为机器人布料模拟不够格发顶会、看不上这类研究，机器人领域又不懂相关计算，未来可能有发展。
+- **国产仿真系统能否替代英伟达生态**：发言者2提出中国是否强依赖英伟达生态的问题；发言者7回应称有朋友宋应赌会被卡脖子、在做国产替代，这是business层面的复杂问题，技术上最终会比较统一，但工作人员不会直接touch这个生意。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/7630</t>
+          <t>21458/7867</t>
         </is>
       </c>
     </row>
@@ -2987,56 +2991,59 @@
       <c r="C7" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审，由最高人民法院组成合议庭公开开庭审理，审判长李少平，审判员魏文超、黄年、王海峰、葛洪涛，法官助理张瑞。庭审围绕三个争议焦点展开：国开行是否善意取得抵押权、罚息复利计算及起算日期、东源煤电及东源煤业是否应连带给付违约金。各方充分发表辩论意见后，合议庭休庭评议并提出调解方案，各方当事人均无异议，同意签署调解协议。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审，由最高人民法院公开开庭审理，审判长李少平，合议庭成员魏文超、黄年、王海峰、葛洪涛，法官助理张瑞。庭审围绕三个争议焦点进行审理：国开行抵押权是否构成善意取得、罚息复利计算及起算日期、东源煤电与东源煤业是否应连带给付违约金。各方充分发表辩论意见后，合议庭休庭评议并提出调解方案，各方均无异议，自愿达成调解协议，法院予以确认并出具调解书。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国开行） | 请求撤销一审判决，改判支持其全部诉讼请求，包括确认抵押权、判令东源煤电及东源煤业连带给付违约金等。 | 主张已按人民银行规定查询融资租赁登记系统，未发现登记记录，已尽审慎义务，构成善意取得；利息、罚息、复利计算有合同依据；东源煤电未配合办理账户管理及柜台前移手续，应支付违约金。 |
-| 被上诉人（东源煤电） | 请求驳回上诉，维持原判。 | 主张国开行未在抵押时点查询融资租赁登记系统，且因借款人与抵押人存在全资控股关系，审查义务应扩大至东源煤电，不构成善意取得；国开行宣布贷款提前到期未给合理期限，罚息不应作为复利计算基数；国开行未举证证明违约行为，无权主张违约金。 |
-| 被上诉人（东源煤业） | 请求驳回上诉，维持原判。 | 主张与东源煤电意见一致，国开行未举证证明其存在违约行为，不应承担连带给付违约金责任。 |
-| 被上诉人（东源曲靖电力） | 请求驳回上诉，维持原判。 | 主张与东源煤电意见一致，国开行未在抵押时点查询融资租赁登记系统，不构成善意取得。 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持原判。 | 主张国开行未在抵押时点查询融资租赁登记系统，不构成善意取得；东源煤电对设备出资系无权处分，电力公司未取得所有权；国开行审查义务应扩大至东源煤电。 |
+| 上诉人（国开行） | 请求撤销一审判决，改判支持其抵押权、罚息复利及违约金主张 | 主张抵押设备为通用设备，无唯一标识码，已对抵押人曲靖电力公司进行融资租赁登记查询且无结果，构成善意取得；利息计算至2017年12月20日，罚息自2018年6月13日发函要求还款之日起算，复利按合同第6条第4款约定计算；依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金，且东源煤电未配合办理账户管理及柜台前移手续。 |
+| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 主张2015年12月2日邮件附件《东源公司融资情况统计表》已用红色标注抵押设备与招银租赁设备名称相同，国开行未尽注意义务；合同约定应限期偿还而非立即偿还，国开行未给予合理期限；罚息不应作为复利计算基数；国开行未举证证明违约行为，且未按合同约定先行限期纠正，无权主张违约金。 |
+| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 主张国开行提供的是2018年9月查询证书而非2015年12月抵押时点查询结果，不符合人行规定；国开行审查义务应扩展至东源煤电；东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权；国开行未在抵押时点查询登记系统，不构成善意取得。 |
 # 举证与法庭调查
 ## 举证与质证
-- **国开行提交**：2018年9月对曲靖电力公司的融资租赁查询证书（第5组证据第1项），证明其已尽查询义务；招银租赁质证认为该查询证书不符合要求，依据中国人民银行2014年93号规定，国开行应在抵押时点（2015年12月）进行融资租赁登记查询。
-- **国开行提交**：证据54页、58页东源煤电公司、曲靖电力公司对案涉设备的权属证明材料及股东会决议，证明抵押设备所有权属曲靖电力公司；招银租赁未对该组证据提出实质性质证意见。
-- **国开行提交**：融资租赁登记核查表（证据108页），证明已对曲靖电力公司名下融资租赁登记进行核查；招银租赁认为核查范围应扩大至东源煤电。
-- **招银租赁提交**：回租设备清单（证据第7页），载明设备名称、生产厂家、出厂日期2012年3月1日，证明案涉设备为融资租赁物；国开行质证认为清单未载明设备型号，且经现场调查核实，抵押设备铭牌生产日期均在2013年以后，无法认定同一设备。
-- **招银租赁提交**：2013年、2015年审计报告（证据82页、95页），证明曲靖电力公司注册资本4亿元已实缴，设备出资事项已载明；国开行质证认为该证据反证曲靖电力公司已取得设备所有权。
-- **东源方提交**：2015年12月2日邮件及附件《东源公司融资情况统计表》，证明已向国开行告知招银租赁对案涉设备享有融资租赁权益；国开行质证认为邮件正文及附表均未载明告知融资租赁情形，且统计表中招银租赁栏记载的抵押类型为不动产抵押，与融资租赁系不同法律概念。
+- **国开行提交**：2018年9月对曲靖电力公司的融资租赁查询证书，证明其已尽查询义务；东源方质证认为该证书不符合要求，根据2014年93号中国人民银行规定，国开行应在抵押时点（2015年12月）进行查询。
+- **国开行提交**：证据54页、58页东源煤电公司、曲靖电力公司对设备的权属证明材料和股东会决议，证明抵押设备所有权属曲靖电力公司；招银租赁未对该组证据提出实质性质证意见。
+- **国开行提交**：证据108页融资租赁登记核查表，证明其已对曲靖电力公司名下融资租赁登记进行核查；招银租赁质证认为核查范围应扩展至东源煤电。
+- **招银租赁提交**：一审证据第7页回租设备清单，载明设备名称、生产厂家，但未载明型号；国开行质证认为该清单无法证明设备唯一性，且清单记载出厂日期为2012年3月1日，与国开行现场调查核实的铭牌生产日期（2013年11月、12月、2014年3月）不符。
+- **招银租赁提交**：2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元已实缴；国开行质证认为该报告已载明设备出资事项，招银租赁应当知道设备出资情况。
+- **东源方提交**：2015年12月2日邮件及附件《东源公司融资情况统计表》，证明已告知国开行抵押设备存在融资租赁情况；国开行质证认为该邮件系贷后审查材料，统计表中招银租赁栏记载抵押类型为不动产抵押，与本案融资租赁是两个法律概念，不能证明已履行告知义务。
 ## 证人/鉴定陈述
 未提及
 ## 法官询问
-- **审判长询问**：各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果？国开行代理人认为系行业强制性规范，旨在防范金融风险；东源方代理人认为系行业指导性规范，不产生物权后果；招银租赁代理人认为系权利公示，可产生对抗效力，但不影响所有权设立转移。
-- **合议庭成员询问**：央行融资租赁登记系统有几种查询方式？国开行代理人称仅能通过单位名称查询；招银租赁代理人称可通过公司名称或设备情况两种方式查询，但设备查询涉及种类物区分问题。
-- **合议庭成员询问**：案涉5套设备登记时是否登记唯一识别码？招银租赁代理人称设备无唯一识别码，非必填项，故未登记；国开行代理人确认设备无唯一识别码。
-- **合议庭成员询问**：国开行贷款前风控资料中是否有内部规定要求必须查询融资租赁登记系统，未查到也需保留查询记录？国开行代理人称无此规定，因未查询到结果故未保留记录。
-- **合议庭成员询问**：国开行认为查询义务是基本义务还是全面审慎义务？国开行代理人认为系基本义务，只需查询抵押人名下登记；招银租赁代理人认为系严格义务，银行未查询即不构成善意。
-- **合议庭成员询问**：若银行通过其他途径知晓动产为融资租赁物，是否仍需查询登记系统？国开行代理人认为基本义务必须履行；招银租赁代理人认为仍需通过央行系统查询，因其他方式无法证明。
-- **合议庭成员询问**：融资租赁司法解释第9条第2款的举证责任如何分担？国开行代理人认为按谁主张谁举证原则；招银租赁代理人认为第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
-- **审判长询问**：各方如何看待不同登记机构产生的登记信息冲突？国开行代理人认为系系统信息不完整、条块分割所致；东源方代理人认为系统整合有必要但提不出成熟建议；招银租赁代理人建议从立法、行业协会、技术操作三个层面解决。
+- **审判长询问**：各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果？国开行认为属行业强制规范，目的是防范金融风险；东源方认为属行业指导性规范，不当然产生物权后果；招银租赁认为非物权登记，但具有对抗效力。
+- **审判员询问**：央行融资租赁登记系统有几种查询方式？国开行称仅能通过查询单位名称查询；招银租赁称可通过公司名称或设备信息查询，但设备查询涉及种类物区分问题。
+- **审判员询问**：案涉5套设备登记时是否登记了唯一识别码？招银租赁称设备无唯一识别码，未登记；东源方补充称初始登记时将租赁物清单作为附件上传，清单载明设备名称、数量、原值、净值、出厂时间、生产厂商及存放地点。
+- **审判员询问**：国开行贷款前风控资料中是否有内部规定要求必须查询融资租赁登记，未查到也需保留记录？国开行称无此规定，因未查询到结果故未保留记录。
+- **审判员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁称非必填项，案涉设备无唯一识别码。
+- **审判员询问**：设备安装后发电机上是否有唯一标识码？招银租赁称铭牌上仅有型号和参数，同型号设备铭牌相同。
+- **审判员询问**：违反查询规范在多大程度上导致融资租赁司法解释第9条第2款法律后果，是基本查询义务还是全面审慎义务？国开行认为系基本义务，仅需对抵押人查询；招银租赁认为系严格义务，未查询即不构成善意。
+- **审判员询问**：若银行通过其他途径知晓动产属融资租赁物，是否无需查询？国开行认为基本义务仍需履行；东源方认为仍需查询以确认权属；招银租赁认为必须通过央行系统查询，因其他方式无法证明。
+- **审判员询问**：融资租赁司法解释第9条第2款举证责任如何分担？国开行认为按谁主张谁举证原则；招银租赁认为第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
+- **审判长询问**：对因不同登记机构产生的登记信息冲突有何意见和建议？国开行认为系系统性问题，建议整合信息；东源方称非专业机构，无成熟建议；招银租赁建议从立法、行业协会、技术操作三层面改进。
 ## 争议焦点与辩论
-### 争议焦点一：国开行是否善意取得抵押权
-- **国开行主张**：其审查义务仅限于抵押人曲靖电力公司，不能扩大到东源煤电公司；案涉设备为通用设备，无唯一标识码，无法通过设备查询融资租赁登记；已按人民银行规定查询融资租赁系统，未发现登记记录，已尽审慎义务，构成善意取得。
-- **东源方主张**：国开行作为专业金融机构，发现抵押设备名称与招银租赁设备完全一致且用红色标注时，应尽到注意义务进行核查；国开行未提供证据证明已做区分，应承担不利后果。
-- **招银租赁主张**：国开行未在抵押时点（2015年12月）查询人行征信中心融资租赁登记系统，不构成善意取得；借款人与抵押人系100%全资控股关系，国开行对东源煤电的审查义务应当具备；东源煤电对设备出资系无权处分，电力公司未取得所有权。
-### 争议焦点二：罚息复利计算及起算日期
-- **国开行主张**：利息计算期间为2017年12月21日至2018年6月12日，利息合计21,795,727.68元；罚息自2018年6月13日计算至2019年2月19日，罚息为41,050,579.57元；复利自2018年3月21日计算至2019年2月19日，复利为1,918,206.23元。
-- **东源方主张**：借款合同约定宣布提前到期需限期偿还，国开行当天发函要求当天偿还，未给合理期限；罚息不能作为复利计算基数，依据《人民币利率管理规定》第21条及最高院判例；复利再计复利无合同依据。
-- **国开行反驳**：东源煤电已构成严重违约，且已进入破产程序，讨论合理期限无意义；合同第6条第4款明确约定对逾期借款利息按罚息利率计收复利，有合同依据。
+### 争议焦点一：国开行抵押权是否构成善意取得
+- **国开行主张**：抵押设备为通用设备，无唯一标识码，无法通过设备查询融资租赁登记；其已对抵押人曲靖电力公司进行查询且无结果，尽到审慎义务，构成善意取得。
+- **东源方主张**：2015年12月2日邮件附件《东源公司融资情况统计表》已用红色标注抵押设备与招银租赁设备名称相同，国开行作为专业金融机构应尽注意义务，进行适当核查。
+- **招银租赁主张**：国开行提供的是2018年9月查询证书，而非2015年12月抵押时点查询结果，不符合人行规定；国开行审查义务应扩展至东源煤电，因其系借款人及抵押人全资控股母公司。
+- **东源方补充**：东源煤电出资行为系无权处分，因招银租赁2012年已取得设备所有权；设备交付到货即取得所有权，招银租赁在交付时点已获所有权。
+- **国开行反驳**：融资租赁登记系行业规范，非物权登记；其审查义务仅限于抵押人曲靖电力公司，不能任意扩大至关联企业。
+### 争议焦点二：罚息复息计算及起算日期
+- **国开行主张**：利息计算期间为2017年12月21日至2018年6月12日，利息合计21,795,727.68元；罚息自2018年6月13日起算至2019年2月19日，罚息41,050,579.57元；复利自2018年3月21日起算至2019年2月19日，复利1,918,206.23元。
+- **东源方主张**：合同约定应限期偿还而非立即偿还，国开行未给予合理期限；罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条及最高院判例；复利再计算复利无合同依据。
+- **国开行反驳**：东源煤电已严重违约且无履约能力，讨论合理期限无意义；合同第6条第4款明确约定对逾期借款利息按罚息利率计收复利，且东源煤电未上诉，一审已支持罚息复利。
+- **东源方再反驳**：合同条款存在歧义，应作不利于格式合同提供方（国开行）的解释。
 ### 争议焦点三：东源煤电、东源煤业是否应连带给付违约金
-- **国开行主张**：借款合同第24条第3项约定违约方应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续，应承担违约责任。
-- **东源方主张**：国开行未举证证明东源煤电存在违约行为，举证不能后果应由其承担；国开行未按合同约定先发出限期纠正函，无权直接主张违约金。
+- **国开行主张**：依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续。
+- **东源方主张**：国开行未举证证明东源煤电存在违约行为，举证不能后果应由其承担；国开行未按合同约定先行发出限期纠正函，无权直接主张违约金。
 # 庭审结果
-本案经合议庭评议，各方当事人自愿达成调解协议，合议庭予以确认并出具调解书。调解方案主要内容：国开行对东源煤电的债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元；招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权，招银租赁对6项设备有所有权，双方对案涉全部发电设备整体盘活处置，变现价款各得50%；调解书生效后20日内，国开行向一审法院申请执行，启动司法处置程序；若司法变现不能，国开行和招银租赁放弃对案涉设备权益，由东源曲靖电力自主生产经营；东源曲靖电力承担案涉设备管理费用，并无条件配合司法处置；一审判决第2项、第4项无争议，按判项内容确认；二审诉讼费用由国开行和东源煤电各承担50%。各方当事人对调解方案均无异议，同意签署调解协议。</t>
+本案经调解结案，各方自愿达成调解协议，法院予以确认并出具调解书。调解方案主要内容：①国开行对东源煤电的债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元；②招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；③国开行对93项设备有抵押权，招银租赁对6项设备有所有权，双方对案涉全部发电设备整体盘活处置，变现款各得50%；④调解书生效后20日内，国开行向一审法院申请执行，启动司法处置程序；⑤若司法变现不能，国开行和招银租赁放弃对案涉设备权益，由东源曲靖电力自主生产经营；⑥东源曲靖电力承担案涉设备管理费用并无条件配合司法处置；⑦一审判决第2项、第4项无争议，按判项内容确认；⑧二审诉讼费用由国开行和东源煤电各承担50%。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>83.8</v>
+        <v>86.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/3560</t>
+          <t>28485/3726</t>
         </is>
       </c>
     </row>
@@ -3193,41 +3200,43 @@
       <c r="C8" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持，合作局领导金昌柱、公司国内领导林总及管理组、技术组参会。验收组于18、19号提前介入项目摸排，20号召开首次会议，分内业、外业两方面对卢萨卡、蒙泽两个点开展检查。卢萨卡点已完成除弹料加工调试以外的所有验收工作；蒙泽点已完成全部验收工作，并顺带完成带料调试和试生产；某皮卡点现场验收尚未开展，内业资料已提前拿到卢萨卡。内业资料基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需完善；外业检查总体评价良好，但存在局部需整改问题。财务方面符合规范。合作局领导要求整改闭环，出报告前完成整改并复核；公司领导要求按合同仔细验收，注意安全。
+本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持并汇报。验收组于18、19号提前介入，20号召开首次会议，对卢萨卡、蒙泽两点开展内业与外业检查。卢萨卡点已完成除带料调试以外的所有验收工作，蒙泽点利用现场资源顺带完成全部验收（含带料调试），姆皮卡点现场验收尚未开展，其内业资料已提前送至卢萨卡。内业检查分管理组和技术组，按合同及规范执行，项目执行团队人员基本在岗，内业资料基本满足标准要求，但分类整理和签字规范性需完善；竣工文件基本达到组卷成册要求，但资料分散，需汇总至卢萨卡。外业检查分建筑、安装、设备三部分：建筑部分原材料集中采购、质量良好，但局部有损伤和排水需检查；安装部分钢结构合格，但监控管线接头有脱落；设备部分运行正常，产能符合设计指标；蒙泽厂区混凝土路面有少量开裂。财务检查符合规范，中基公司无挪用资金情况。验收组提出整改要求，管理组田组长和技术组龚总承诺会后落实，合作局领导金昌柱要求出报告前完成整改并复核。项目有动用不可预见费情况，需完善证据资料，后续专项对接。
 # 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作 | ✅已完成 |
-| 蒙泽点验收 | 已完成全部验收工作，并顺带完成带料调试和试生产 | ✅已完成 |
-| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡 | ⏸未开始 |
-| 内业资料检查 | 基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需完善 | 🔄进行中 |
-| 外业检查-建筑部分 | 原材料使用符合合同要求，主材从国内采购或从卢萨卡集中采购，内在品质和外观质量达到较好标准 | ✅已完成 |
-| 外业检查-安装部分 | 钢结构材料从国内定制，施工工艺和外观质量满足规范标准 | ✅已完成 |
-| 外业检查-设备部分 | 设备参照中国标准定制，厂家高峰期派十几名人员现场指导安装，蒙泽点已进行投料试运行，运行正常，产能符合设计指标 | ✅已完成 |
-| 机电设备安装 | 符合国家质量检验标准 | ✅已完成 |
-| 财务检查 | 财务账户设置、资金往来、银行开户等符合财务处理规范和标准，中基公司无挪用资金情况 | ✅已完成 |
+| 卢萨卡点验收 | 已完成除带料调试以外的所有验收工作 | ✅已完成 |
+| 蒙泽点验收 | 利用现场资源顺带完成全部验收，含带料调试，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
+| 姆皮卡点验收 | 现场验收尚未开展，内业资料已提前送至卢萨卡 | ⏸未开始 |
+| 内业资料 | 基本满足标准要求，但分类整理和签字规范性需完善；竣工文件基本达到组卷成册要求，但资料分散，需汇总至卢萨卡 | 🔄进行中 |
+| 外业检查-建筑 | 原材料集中采购、质量良好，但局部有损伤和排水需检查 | 🔄进行中 |
+| 外业检查-安装 | 钢结构安装合格，但监控管线接头有脱落 | 🔄进行中 |
+| 外业检查-设备 | 设备运行正常，工艺流程满足生产要求，产能符合设计指标 | ✅已完成 |
+| 财务检查 | 账户设置、资金往来、银行开户等符合规范，中基公司无挪用资金情况 | ✅已完成 |
 # 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 蒙泽厂区混凝土路面开裂 | 高 | 非主要通道混凝土路面有少量开裂，可能影响交付后使用，移交外方后可能大面积开裂 | 王总（牵头追溯成因） | 会同相关单位做专题技术研究，分析成因，制定切实可行整改方案，出报告前完成整改，验收组复核 |
-| 监控管线接头脱落 | 中 | 设备启动震动导致管线接头脱落，可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
-| 提升桶位置雨水倒灌风险 | 中 | 赞比亚雨量大、风大，雨水可能倒灌，影响设备运行 | 施工组 | 检查原设计，必要时增加覆盖面积等技术措施 |
-| 廊桥竖条不足 | 中 | 卢萨卡点廊桥端头横向仅三个竖条，可能影响巡检维护人员安全 | 施工组 | 建议中间再加两个竖条，做最后检查和完善 |
-| 人员履约及护照问题 | 中 | 个别同志进出场时间及护照需完善，个别岗位人员申请更换，影响验收报告闭合 | 管理组、技术组 | 完善资料，与国内人力资源对接确认证件延期情况 |
-| 特种人员证件有效期 | 中 | 个别特种人员证件有效期可能未及时更新 | 执行单位 | 与国内人力资源对接，确认延期或更新情况 |
-| 内业资料分类整理和签字规范性 | 中 | 分类整理和签字规范性需完善，影响竣工文件组卷 | 执行单位 | 按规范汇总到卢萨卡，分类成册，按竣工文件归档要求组卷 |
-| 成品保护疏忽 | 中 | 工程实体完工时间较长，成品保护有疏忽，可能有破损 | 施工方 | 移交外方前继续做好成品保护，及时修补破损 |
-| 姆皮卡路途交通安全 | 高 | 姆皮卡路况不好，雨季交通风险高 | 验收组 | 注意交通安全及疫情防控，安全完成验收任务 |
+| 蒙泽厂区混凝土路面开裂 | 中 | 可能影响项目移交后使用，存在大面积开裂隐患 | 管理组、总包单位 | 分析开裂原因，制定科学合理的整改方案，出报告前完成整改并复核 |
+| 监控管线接头脱落 | 中 | 可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
+| 卢萨卡点提升桶位置雨水倒灌 | 中 | 雨水可能倒灌，影响设备运行 | 施工组 | 检查并考虑增加覆盖面积或采取技术措施解决 |
+| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照及证件有效期需完善，影响验收报告闭合 | 管理组、技术组 | 完善人员统计和护照证书收集，与国内人力资源对接 |
+| 内业资料分散 | 中 | 资料分散，未集中组卷，影响竣工文件归档 | 技术组 | 验收完成后第一时间将三个厂区资料汇总至卢萨卡，分类组卷及编码 |
+| 姆皮卡点路途遥远、交通状况不佳 | 高 | 存在交通安全风险 | 验收组 | 注意交通安全，做好疫情防控 |
+| 疫情及雨季影响 | 中 | 影响验收工作进度 | 验收组 | 注意疫情防控，雨季前完成排水检查 |
 # 后续计划
-会后管理组田组长与技术组龚总将验收组提出的问题细化、再检查，通过方案处理解决。技术组承诺：收集所有参与项目现场人员的护照证书；内业资料严格按验收组要求及援外项目执行手册管理办法，在验收完成第一时间将三个厂区资料汇总于卢萨卡，分类组卷及编码；现场实体整改按方案编制要求逐一整改落实。合作局领导要求蒙泽厂区混凝土路面开裂问题在出报告前完成整改，验收组复核形成闭环；工程实体完工时间较长，需继续做好成品保护，及时修补破损。验收组将安排某皮卡点现场验收工作，并继续跟踪不可预见费使用资料完善。</t>
+- **会后整改**：管理组田组长承诺会后与技术组一起细化验收组提出的问题，制定方案并落实整改；技术组龚总承诺在验收完成后第一时间将三个厂区资料（含竣工图）汇总至卢萨卡，分类组卷及编码，并针对现场实体整改按方案逐一落实。
+- **混凝土路面开裂整改**：合作局领导金昌柱要求管理组和总包单位共同分析开裂原因，制定科学合理的整改方案，*在出报告前完成整改*，验收组需进行复核。
+- **资料汇总**：技术组需在验收完成后第一时间将三个厂区资料汇总至卢萨卡，分类组卷及编码。
+- **不可预见费**：验收组将利用后续时间对不可预见费使用情况做专项对接，完善依据证据和数据，确保充分无误。
+- **姆皮卡点验收**：会后将及时安排姆皮卡点现场验收工作，*该点路途遥远、交通状况不佳，需注意交通安全和疫情防控*。
+- **成品保护**：在移交外方前继续做好成品保护，对破损部位及时修补。</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>66.09999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/1889</t>
+          <t>11110/1846</t>
         </is>
       </c>
     </row>
@@ -3438,107 +3447,63 @@
       <c r="C9" t="inlineStr">
         <is>
           <t># 发布会概况
-中金公司策略组于周一上午召开宏观策略周会，由策略组主持人刘刚凯文主持，面向投资者及客户，围绕大美丽法案、关税更新、港股流动性三大宏观议题展开汇报，并邀请公用事业风光首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就光伏反内卷、人形机器人、游戏板块进行行业分享。会议旨在汇报宏观策略观点及行业板块投资机会，整体基调为：宏观层面强调信用周期框架下大美丽法案短期带来流动性压力但中长期有利，关税影响可控且市场逐渐脱敏，港股流动性边际收紧但基本面可盖过影响；行业层面建议在结构性行情中于合适位置提前布局长期正确板块。
+本次中金宏观策略周会于周一上午以线上形式举行，由中金公司策略组刘刚凯文（Kevin）主持，面向投资者与客户。会议围绕海外市场与国内产业两大主线展开：海外部分重点解读“大美丽法案”对美国经济、美股美债及美元流动性的影响，并更新关税谈判进展与港股流动性分析；国内部分则聚焦“反内卷”政策对光伏行业的影响，以及人形机器人、游戏板块（AI应用）的结构性投资机会。公用事业风光首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就相关板块作专题分享。会议整体基调偏积极，认为美股美债波动提供再配置机会，同时建议在结构性行情中提前布局长期方向正确的板块。
 # 核心信息
-- **大美丽法案三大内容**：提高债务上限约5万亿美元（消除违约风险、恢复政府融资能力）；延长2017年减税法案（非新增减税，避免年底自动加税，每年额外支出约3400亿美元、总计3.4万亿美元，同时削减新能源补贴等支出1.4万亿美元）；取消899条款（取消海外投资者持有美债的利息所得税，消除美元体系根基担忧）。
-- **赤字率测算**：关税收入每年约3000–4000亿美元，可覆盖每年3400亿美元额外支出，财政赤字率基本维持5–6%，不会大幅增加。
-- **美债供给与利率**：7–9月财政部需发债约1万亿美元（参考2023年三季度发债1万亿美元推高美债利率从3.8%升至5%、美元走强、美股小幅下跌4–5%）；本次期限溢价已处于2013年以来高位，利率抬升幅度或不及2023年，但存在再配置机会。
-- **美元与美股判断**：四季度美元可能小幅走强、美股可能反弹跑赢，核心依据为信用周期（政府、AI产业投资、私人部门需求三因素）环比改善；三季度需过坎（大美丽法案流动性影响、关税、7月FOMC会议、7–8月通胀边际走高、中报业绩期）。
-- **关税四点判断**：① 关税大概率会做（用于支撑收入）；② 需维持一定税率（当前豁免10%水平即可收3000–4000亿美元）；③ 不能太高（过高通胀受不了）；④ 市场逐渐脱敏、静观其变（视为谈判技巧）。
-- **关税新变化**：时间拖后（原7月9日达成）；相比4月2日对等关税水平大部分回落（除巴西可能大幅增加）；加拿大、墨西哥、欧盟单拎谈判（贸易占比高，其余国家占比可忽略，最高日本仅4.5%）；有效税率当前约10–12%，8月1日全回去则10–15%，最极端18%。
-- **关税对通胀与美联储**：通胀压力缓慢抬升，年底约3.3–3.4%；即便18%有效税率也不大幅改变通胀路径；7月降息勉强，9月及四季度后可降。
-- **对华关税与转口限制**：对华关税约40–50%（2018年约20%为基数）；越南协议转口限制40%、英国协议亦有转口限制，均低于对华税率；关注8月1日其他市场谈判及8月12日中美谈判进展。
-- **港股流动性**：5月后微观流动性释放（HIBOR大幅下降，金管局投放大量资金）；港币触及7.85，金管局将收紧流动性（可小幅收如收90亿、放1000多亿延缓收紧速度）；三季度流动性供给不如二季度（美元流动性供给压力＋港币未回＋IPO融资较多）；港股点位23000–24000区间震荡。
-- **港股风格建议**：长期方向两头分红（短期银行股溢价低于20%，股息率扣税后优势不大；短期1.25%为隐形底）；成长端新消费较拥挤、创新药稍降、科技硬件AI应用较3月大幅下降可提前埋伏；中期关注创新药、人形机器人、AI应用、短视频生成、软件催化剂。
-- **光伏行业供需失衡**：全球新增光伏装机从2020年130GW增至2024年530GW（4年CAGR 42%）；2025–2026年全球需求增速预计回落至10%左右（基数变大＋电网平衡制约）；2023年产能从600GW增至1000GW；2025年全球需求650–700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍。
-- **光伏价格与亏损**：2022年以来产业链价格下跌70–90%；硅片电池自2023年四季度亏损，硅料组件自2024年二季度正式亏损；持续亏损下尚未见企业退出。
-- **反内卷政策时间线**：2024年5月17日光伏行业协会在工信部电子信息司指导下召开光伏行业高质量发展座谈会（强调市场化手段＋政府有形手，提出产能建设指导管理、保护新技术、打击低于成本销售、鼓励兼并重组）；2024年10月、12月企业减产自律座谈会（收效不明显）；2025年2月国常会提出化解重点产业结构性矛盾；6月29日起连续5天上层三次发声（人民日报《在破除内卷式竞争中实现高质量发展》，指出光伏高投入低产出、阶段性供需错配、高标准市场体系尚待健全、地方政绩观错位）；7月1日总书记主持中财委第6次会议（依法依规治理企业低价无序竞争、引导产品品质、推动落后产能退出）；7月3日工信部召开光伏企业座谈会（传达光伏产业重要性、党中央重视程度、破除反内卷迫切性，指出技术创新与产业产能升级是重要手段）。
-- **硅料环节整合判断**：集中度最高（在产企业不到20家）；成本曲线最陡峭（2025年丰水期边际现金成本约38元/公斤，颗粒硅约28元/公斤，尾部厂商高达45元/公斤）；供需比超200%（高于硅片电池组件150%左右）；作为最上游影响全产业链定价，整合最迫切。
-- **电池与组件环节**：电池环节供需最良好（500GW PERC资产基本退出，TOPCon占90%市场份额，BC技术单月渗透率提升至5–6%）；组件环节分散（企业几十上百家，部分有独特海外市场），整合较难。
-- **光伏玻璃产能出清**：2024年9月第一波产能出清（有效产能降幅约6%）；协会呼吁降产保价，7月开始第二轮产能出清（参加企业计划降产30%）；需出清约2万吨方可修复供需平衡；今年价格已创历史新低，龙头企业经营性成本约1元/平方米，后续不排除亏损幅度加大。
-- **光伏价格与市场反应**：多晶硅期货价格上周五触及40元/公斤（前一周现货约35元/公斤，上周报价大幅上涨）；硅片报价涨约10%、电池涨约2分钱；过去两周硅料和玻璃股价上涨20–30%、组件涨幅约10%靠后；组件跟涨意愿受下游电站136号文（新能源全面入市）电价不确定性制约，需观望招标情况。
-- **穿越周期企业特征**：头部一体化组件企业议价能力宝贵（收现款再发货、占用上游账期获正向经营现金流，财务压力小于上游）；低杠杆强现金强融资能力企业（部分资产负债率仅10%出头，2023–24年资本开支谨慎）；持续技术创新（颗粒硅使用比例从10–20%提升至50%、硅片薄片化、钨丝导入、浆料铜替代银2025–26年大规模导入、TOPCon取代PERC）。
-- **人形机器人二季度表现**：A股机器人板块4–6月按流通市值加权平均跌约9%，跑输机械设备板块约12个百分点；特斯拉核心供应商标签股从3月高点普遍回调30–40%；5–6月交易型资金止损明显；回调主因特斯拉4月后宣布量产时间线延后＋中美关税降低风险偏好。
-- **华为云生态主线**：6月底华为开发者大会首发盘古世界模型（时空可控生成技术，首个支持点云和视频双模态同时生成的大模型，解决训练物理模型痛点）；CloudRobot平台构建三大能力（多模态生成模型提供泛化训练环境、规划大模型自主决策、执行大模型将操作精度提升至毫米级）；华为明确不造机器人，以RTC方式开放，探索AI agent收费或license收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作。
-- **本土企业技术闭环主线**：智元机器人拟通过收购控股材料厂商在A股上市（具备AI＋双足及轮式人形机器人全栈能力，合作零部件厂商股价底部异动）；宇树科技年收入突破10亿元、下半年有望加速上市；智元、宇树同时中标中国移动旗下接近1.2亿元人形机器人采购订单（部署移动营业厅与消费者互动）；国内人形机器人本体厂商至少100家以上；物流端为投资回报率较明确场景（降低单件运输成本为2025年下游刚需）。
-- **特斯拉延期与硬件替代主线**：Optimus存在电机过热、灵巧手负载不足、续航问题，整体变更方案并筛选供应商；电机过热对应无框力矩电机新品发布（改善散热性能）；续航问题对应轻量化方向（以塑代钢、替代铝合金）；建议聚焦电机硬件优化窗口。
-- **港股机器人板块**：二季度呈现明显估值溢价（PE、PS均显著）；来源为稀缺性溢价＋流动性红利（进入港股通或相关指数后享受全球科技型资金关注）；下半年港股机器人板块确定性扩容，关注A＋H动向。
-- **三季度三类关注信号**：华为云生态接入厂商三季度继续新增；头部企业出货量跨越年化500台或1000台（关注股价及供应商演绎）；聚焦电机硬件优化窗口；技术创新、产业需求、工厂替代三重周期共振孕育投资机会。
-- **游戏政策环境**：去年黑神话悟空爆火后游戏行业文化价值与经济价值获广泛认可，政策支持力度达空前高度；今年1月、3月国务院层面对传媒板块发布游戏行业支持政策；广东、浙江、北京、上海等地出台专门政策支持包（中小微企业奖励、数字内容文化产业出海支持、IP方向）。
-- **版号发放数据**：去年四季度以来版号每月正常发放，今年每月同时发放国产与进口网络游戏版号；6月单月发放158个（国产147个、进口11个），为2018年以来单月最高水平。
-- **游戏市场规模**：2022年以来增速红线约0%（版号停发时降至0以下）；2024年8月以来单月持续正增长；今年1–5月游戏市场规模同比增长17%（1400多亿元），手游同比增长20%。
-- **新品周期与预期差**：年初市场预期今年缺乏产品大作（腾讯、网易上半年和下半年重点产品相对小，米哈游无特别重磅作品）；中型厂商新品成为A股及港股中型公司核心催化——吉比特5–6月上线的《仗剑传说》首月流水2亿多、边际带动强；巨人网络《超自然行动组》6月预估流水过亿、年化乐观约20亿元、利润提升50%以上；大厂缺少大体量产品时中型厂商获客友好（对比去年员工与蛋仔竞争推高流量价格），国内大多数新游用户ROI良好。
-- **游戏板块估值**：TTM PE约30倍（2023年AI行情下到过45倍）；2025年静态PE约20倍、明年更低；板块与两年前不同（悦己型消费领域、受宏观经济影响小、1–5月同比增长17%、新品不受限、逆周期性）；政策支持长周期运营；企业反腐与组织架构调整提升新品推出效率与胜率；新品利润滞后性（今年上新利润明年兑现），明年业绩确定性提供估值支撑。
-- **游戏板块跟踪指标**：关注新品市场表现、用户获取下载榜排名等领先指标；短期板块估值提升仍有较大空间，市场对利润预期有修正增长，最终实现戴维斯双击；下半年及明年新品（网易、腾讯等更多落在明年大周期）。
+## 大美丽法案与美股美债展望
+- **法案三大块**：提高债务上限约5万亿美元；延长2017年减税法案（非新增减税，避免年底自动大幅加税）；取消899条款（此前拟对海外投资者持有美债利息所得征税，取消后消除主权基金抛售美债担忧）。
+- **财政收支测算**：延长减税每年额外支出约3400亿美元（合计3.4万亿美元），同时削减其他支出（含减少新能源补贴1.4万亿美元）；关税收入每年约3000–4000亿美元可覆盖额外支出，测算赤字率基本维持5%–6%，不会升至7%以上。
+- **三季度流动性抽水**：债务上限提高后财政部需发债并回补TGA账户，预计额外供给约1万亿美元；参考2023年三季度发债1万亿美元推高美债利率从3.8%升至5%、美元走强、美股小幅下跌4%–5%，本次期限溢价已处2013年以来高位，利率上行幅度或不及2023年，但7–9月美元流动性边际收紧。
+- **美股表现与信用周期**：纳斯达克自4月底底部反弹35%，市场对「股债汇三杀」「去美元化」担忧过度；信用周期框架下美国经济环比改善（低基数），中国面临高基数压力，四季度美元可能小幅走强、美股可能反弹跑赢。
+- **配置建议**：美股美债波动提供再配置机会，不悲观但当前位置性价比不高；三季度需过坎包括大美丽法案流动性影响、关税、7月FOMC会议、7–8月通胀边际走高及中报业绩期。
+## 关税政策更新
+- **四点判断**：关税大概率实施以支撑收入；需维持一定税率（当前豁免10%水平即可收上来3000–4000亿美元）；税率不能过高否则通胀受不了；市场逐渐脱敏、静观其变，高税率威胁可能是谈判技巧。
+- **有效税率测算**：当前有效税率约10%–12%；若8月1日关税全回去甚至提高，有效税率回到10%–15%，最极端约18%；对通胀影响有限，年底通胀可能升至3.3%–3.4%，不大幅改变通胀路径。
+- **谈判进展与时间表**：原定7月9日达成的时间变相拖后；除巴西外大部分国家税率相比4月2日对等关税水平回落；加拿大、墨西哥、欧盟贸易占比高需单独谈妥，其他国家即便税率翻倍对有效税率影响很小（最高日本占比4.5%）。
+- **对华关税与转口限制**：对华关税约40%–50%（2018年约20%为基数）；越南、英国达成的协议均含转口限制（越南转口限制40%），需关注8月12日中美谈判进展及转口限制影响。
+## 港股流动性
+- **流动性现状**：5月后微观流动性释放，HIBOR大幅下降（金管局投放大量资金），港币触及7.85弱方兑换保证；金管局不会放弃联系汇率制度（7.75–7.85区间），会小幅收紧（如收90亿、放1000多亿）以延缓利率收紧速度。
+- **三季度流动性判断**：美元流动性供给压力（7–9月美债供给）叠加港币未完全回升，三季度流动性供给不如二季度；IPO融资较多也形成约束；港股指数在23000–24000区间震荡，上不去也下不来。
+- **风格与配置**：长期方向仍是「两头分红」——银行股溢价已低于20%（除保险外扣税后股息率优势不大，短期透支），但相比国债利率仍有空间，短期12.5%是隐形底；成长端新消费较拥挤、创新药有所回落，科技硬件与AI应用拥挤度相比3月大幅下降，可提前布局创新药、人形机器人、AI应用、短视频生成、软件等方向。
+## 反内卷与光伏行业
+- **行业供需失衡**：全球新增光伏装机从2020年130GW增至2024年530GW（4年复合增速42%），2025–2026年增速预计回落至10%左右（基数变大、电网平衡制约）；2025年全球需求预计650–700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍。
+- **价格与盈利**：2022年以来产业链价格下跌70%–90%；硅片电池自2023年四季度亏损，硅料组件自2024年二季度亏损；持续亏损下尚未见企业退出，未来两年需求难以消化现有产能。
+- **反内卷政策升级**：2024年5月17日光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会（强调市场化手段+政府有形手）；2025年2月国常会提出化解重点产业结构性矛盾；6月29日起连续发声——`人民日报`发文《在破除内卷式竞争中实现高质量发展》、7月1日中央财经委第6次会议提出依法依规治理低价无序竞争、推动落后产能退出、7月3日工信部召开光伏企业座谈会；具体干预措施尚未披露。
+- **硅料环节整合最迫切**：在产企业不到20家、集中度高；成本曲线最陡峭（丰水期边际现金成本约38元/公斤，颗粒硅约28元/公斤，尾部厂商高达45元/公斤）；供需比超200%（高于其他环节150%左右）；作为最上游影响全产业链定价。
+- **价格与市场反应**：多晶硅期货价格上周五触及40元/公斤（前一周现货约35元），现货报价大幅上涨，前期已签订单执行力度增强；硅片报价上涨约10%、电池涨约2分钱；过去两周硅料和玻璃股价上涨20%–30%，组件涨幅约10%靠后；组件跟涨需观望下游电站招标（受136号文新能源全面入市影响电价不确定性增加）。
+- **光伏玻璃产能出清**：2024年9月第一轮产能出清有效产能降幅约6%；协会呼吁降产保价，企业计划7月起降产30%，测算需出清约2万吨方可修复供需平衡；当前价格创历史新低，龙头企业经营性成本约1元/平方米，亏损幅度可能进一步加大。
+- **穿越周期能力**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流；低杠杆、强现金、强融资能力企业财务健康（部分资产负债率仅10%出头）；技术变革包括颗粒硅使用比例从10%–20%提升至50%、硅片薄片化与细线化、钨丝全面导入、电池浆料铜替代银（2025–2026年大规模导入）、TOPCon电池取代PERC（PERC基本退出市场，BC技术单月渗透率提升至5%–6%）。
+## 人形机器人
+- **二季度板块表现**：A股机器人板块4–6月按流通市值加权平均下跌约9%，跑输机械设备板块约12个百分点；特斯拉核心供应商标签股自3月高点普遍回调30%–40%；5–6月交易型资金止损明显；回调主因是特斯拉4月后宣布量产时间线后移叠加中美关税降低风险偏好。
+- **华为链技术突破**：6月底华为开发者大会首发盘古世界模型（时空可控生成技术，首个支持点云和视频双模态同时生成的大模型，解决物理模型训练痛点）；CloudRobot平台构建三大能力——多模态生成模型（泛化训练环境）、规划大模型（复杂物理世界自主决策）、执行大模型（操作精度提升至毫米级）；华为明确「不造机器人」，以RTC方式开放，探索AI agent收费或license收费模式；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作。
+- **本土企业进展**：智元机器人拟通过收购材料厂商在A股上市（具备AI+双足及轮式人形机器人全栈能力），相关零部件厂商股价底部异动；宇树科技年收入突破10亿元，下半年有望加速上市；智元与宇树同时中标中国移动近1.2亿元人形机器人采购订单，将部署于移动营业厅与消费者互动；国内人形机器人本体厂商超100家，物流端降低单件运输成本是2025年下游明确刚需。
+- **特斯拉延期与硬件替代**：Optimus存在电机过热、灵巧手负载不足、续航问题，特斯拉正在变更方案并筛选供应商；电机过热对应无框力矩电机散热改善新品发布，续航问题对应轻量化方向（以塑代钢、替代铝合金）；特斯拉暴露的硬件瓶颈是行业共性瓶颈，构成硬件替代窗口期。
+- **港股估值与三季度信号**：二季度港股机器人板块PE、PS估值溢价明显（港股通纳入后享受全球科技资金关注），下半年港股板块确定性扩容，关注A+H动向；建议关注三类信号——华为云生态接入厂商三季度新增趋势、头部企业出货量跨越年化500台或1000台、电机硬件优化对应的零部件窗口。
+## 游戏板块
+- **政策与版号**：6月单月版号发放158个（国产147个、进口11个），为2018年以来单月最高；自去年四季度起版号每月正常发放，今年起每月同时发放国产与进口版号；国务院层面1月、3月发布游戏行业支持政策，广东、浙江、北京、上海等地出台专项政策包（含中小微企业奖励、数字内容文化产业出海支持、IP方向）。
+- **市场规模**：2025年1–5月游戏市场规模同比增长17%（1400多亿元），手游同比增长20%；自2024年8月起单月持续正增长（版号停发时期增速曾降至零以下）。
+- **新品周期**：年初市场预期今年缺乏大作（腾讯、网易重点产品较少，米哈游亦无重磅作品），但中型厂商新品成为A股、港股核心催化——吉比特《仗剑传说》5–6月上线首月流水2亿多元，巨人网络《超自然行动组》6月流水过亿（乐观年化约20亿元，利润提升50%以上）；中型厂商获客ROI普遍良好；三七《斗罗》等新品7月上线，网易、腾讯等大厂新品更多落在明年。
+- **估值与展望**：游戏板块TTM PE约30倍，2025年静态PE约20倍（切明年更低），低于2023年AI行情时的45倍；新品利润有滞后性（今年上线新品利润明年兑现），表观估值不便宜但明年业绩确定性提供支撑；建议跟踪新品市场表现、用户获取下载榜排名等领先指标；板块自6月24日起半个月涨幅最猛，近期出现调整，判断为回调而非行情结束，在消费、政策、新品周期三重利好下有望调整后实现戴维斯双击。
 # 官方表态
-**中金公司策略组**（刘刚凯文）就宏观议题主动表态：
-## 大美丽法案与美元资产
-- **对去美元化共识的质疑**：不认同「去美元化」这一高度趋同的共识，认为其基于宏大叙事，无法确定兑现时间（是10年后还是今年内），不应以长期逻辑影响短期配置；4月底若按「股债汇三杀」逻辑操作，会错过纳斯达克自底部反弹35%的行情。
-- **对市场两大误区的纠正**：一是把美元弱当成去美元化——美元走弱可因美联储降息预期升温等多种原因；二是把美元弱和美股弱直接划等号——美元弱在多数时候（非抛售美国资产的情形）对美股有利，因其海外收入占比高、可形成金融条件宽松，甚至可能出现美元小幅走强、美股再度跑赢的情形。
-- **对信用周期的判断**：基于信用周期分析，美国经济如「烧篝火」不泼冷水即可自然修复，上半年遭遇DeepSeek冲击、财政收缩、对等关税三盆冷水；中国如「煮水」需持续添柴，添柴速度变慢水温会降。下半年美国形成低基数、可能环比改善，中国面临高基数，或形成边际上的此消彼长。
-- **对大美丽法案的定性**：不能严格称为减税法案，因没有新增减税，大部分是延长2017年既有减税法案；若不延长，今年底将出现大幅加税，对居民收入、消费和经济有明显影响。
-- **对债务上限提高的解读**：提高约5万亿美元债务上限消除了违约风险，使其可以花钱；若花钱花到刀刃上可提振部分增长；不能假设GDP不增长，否则债务占GDP比例会高到135%。
-- **对财政赤字的测算**：延长减税每年额外支出约3400亿美元（总计3.4万亿美元），但关税收入每年约3000–4000亿美元可覆盖，财政赤字不会大幅增加，赤字率基本维持在5–6%，大体相抵；关税因此一定要做，否则收不上钱、赤字大幅增加。
-- **对三季度流动性压力的提示**：7–9月财政部需发债约1万亿美元并回补TGA账户，带来额外供给；参照2023年三季度发债1万亿推高美债利率从3.8%升至5%、美元走强、美股小幅下跌4–5%的经验，本次供给确定增加，但需求端可能对冲；期限溢价已处2013年以来高位，美债利率未必抬升到5%以上。
-- **对美股美债的配置建议**：重申对美股并不悲观，但当前涨至高位、预期打得较多，性价比不高；若出现波动，依然是提供再配置的机会，波动后（流动性供给压力释放后）有再配置机会。
-## 关税
-- **对关税走势的四点判断**：第一，关税大概率要做，用于支撑收入、支撑支出；第二，需维持一定税率才能收上钱，现在豁免10%的关税水平即可收上来3000–4000亿，不需要弄太高；第三，不能太高，太高通胀受不了；第四，市场逐渐脱敏、静观其变，威胁提高税率有可能是谈判技巧。
-- **对关税新变化的解读**：时间变相拖后（原定7月9日达成）；相比4月2日对等关税水平大部分回落，除巴西外并未大幅增加；加拿大、墨西哥、欧盟贸易占比太高需单独谈妥，其他国家即便增加一倍也不影响有效税率（最高日本占比仅4.5%）。
-- **对有效税率的测算**：当前有效税率约10–12%（豁免税率水平）；若8月1日全部恢复甚至更高，最多回到10–15%，最极端回到18%；即便18%也不大幅改变通胀路径，通胀到年底缓慢抬升至3.3–3.4%左右。
-- **对关税谈判性质的判断**：根据其自身约束（股债汇三杀、中期选举临近、收钱目的只需10–12%有效税率），姑且认作谈判技巧；威胁提高是谈判筹码。
-- **对华关税与转口限制的提示**：对华关税约40–50%（2018年约20%为基数）；越南、英国达成的协议均有转口限制，越南转口限制为40%，比对华税率还低；需关注8月12日中美谈判进展及转口限制。
-## 港股流动性
-- **对港股流动性的判断**：美元美债利率并非绝对主导港股市场的唯一变量，自身基本面强完全可以盖过其影响；美元流动性供给压力叠加港币未完全回升，三季度流动性供给不如二季度，IPO融资较多也形成约束。
-- **对港币汇率与金管局的解读**：金管局投放大量资金使HIBOR大幅下降、流动性强，但港币触及7.85；联系汇率制度一定是最优先考虑，金管局一定会收（流动性），但可小幅收（如收90亿、放1000多亿）以延缓利率收紧速度；从边际上讲流动性相比5月、二季度之后一定变紧。
-- **对港股点位的判断**：一直提示市场点位在23000–24000区间，过去一两个月指数在此区间上不去、下也未必下得来；不波动很难提供提前埋伏预期没那么强的下一个风格的机会。
-- **对投资节奏的建议**：低迷时积极介入，亢奋时适度锁定利润；在合适的位置拿长期正确的板块。
-**中金公司公用事业风光首席分析师刘佳妮**就光伏反内卷表态：
-## 光伏反内卷
-- **对政府干预必要性的判断**：在行业持续亏损但尚无企业退出的情况下，期待政府干预，认为有一定必要性；未来两年全球需求增速回落至10%左右，现有产能无法被消化。
-- **对反内卷政策升级的解读**：2025年反内卷力度和政策级别进一步提升——2月国常会提出化解重点产业结构性矛盾；6月29日起连续5天上层三次发声（人民日报《在破除内卷式竞争中实现高质量发展》指出光伏高投入低产出、阶段性供需错配、高标准市场体系尚待健全、部分地方政绩观错位等问题）；7月1日总书记主持召开中财委第6次会议提到依法依规治理企业低价无序竞争、引导产品品质、推动落后产能退出；7月3日工信部再度召开光伏企业座谈会，传达光伏产业重要性、党中央重视程度及破除反内卷的迫切性，指出技术创新、产业产能升级是重要手段。
-- **对价格恶性竞争的判断**：随着反内卷力度不断强化升级，价格恶性竞争有望告一段落，至少夯实行业底部。
-- **对硅料环节整合的判断**：硅料环节最易切入反内卷——集中度在四个环节中最高（在产企业不到20家）；成本曲线最为陡峭（当前丰水期行业硅料边际现金成本约38元/公斤，颗粒硅约28元，尾部国内厂商高达45元）；供需比超过200%，高于其他环节150%左右；作为最上游影响整个产业链定价，整合最为迫切。
-- **对下游整合难度的判断**：下游电池和组件相对分散（组件企业几十上百家，部分靠独特海外市场生存），行业整合相对困难；电池环节供需情况最为良好（500GW PERC电池资产基本退出，TOPCon占90%市场份额，BC技术单月渗透率提升至5–6%）。
-- **对光伏玻璃的判断**：光伏玻璃协会呼吁降产保价，已自发开始第二轮产能出清，参加企业计划7月份降产30%；测算国内光伏玻璃产能需出清约2万吨方可修复供需平衡；当前价格已创历史新低，龙头企业经营性成本约1元/平方米，后续不排除亏损幅度进一步加大、逐步推动行业出清。
-- **对行业价格企稳的判断**：官媒发声、中财委会议及工信部座谈会后，多晶硅期货价格大幅反弹，截止上周五触及40元/公斤；现货价格较前一周35元左右大幅上涨；前期已签订单执行力度明显增强，硅料市场呈现触底企稳态势；硅片报价上涨约10%，电池上涨约两分钱；组件价格有跟涨意愿，但下游电站受136号文（新能源全面入市）影响、电价不确定性增加，能否接受涨价传导需观望招标情况，过去两周组件涨幅相对靠后（约10%）。
-- **对穿越周期企业的判断**：头部一体化组件企业可通过收现款再发货、占用上游供应商账期获得正向经营现金流，穿越周期能力相对较强、财务压力小于上游；关注低杠杆、强现金、强融资能力企业（部分资产负债率仅10%出头）；技术创新和成本竞争是行业不变主旋律——颗粒硅使用比例从10–20%提升到50%、硅片薄片化、钨丝全面导入、电池浆料铜替代银将在2025–26年大规模导入、TOPCon取代PERC，这些技术变革无关反内卷政策最终如何，都会帮助企业穿越周期。
-**中金公司机械军工分析师郭文秀**就人形机器人表态：
-## 人形机器人
-- **对三季度主线的判断**：三季度人形机器人将围绕三条主线展开——华为云生态开放、本土人形机器人企业技术闭环、特斯拉延期带来的硬件替代窗口期。
-- **对华为链技术突破的判断**：华为在2025开发者大会首发盘古世界模型，通过时空可控生成技术实现2D视频模态和3D激光点云模态像素级对应，成为首个支持点云和视频双模态同时生成的大模型，可用来训练智驾和机器人；CloudRobot平台构建三大基础能力——多模态生成模型（提供泛化训练环境）、规划大模型（帮助自主决策）、执行大模型（操作精度提升到毫米级）。
-- **对华为商业模式的解读**：华为明确强调不造机器人，以打破机器人本体厂商和系统集成商的合作焦虑；愿意以RTC方式向全社会开放，未来有望探索类似AI Agent收费或License收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作，云智能加场景深耕模式有望下半年看到更多。
-- **对本土企业资本运作的判断**：智元机器人企图通过收购方式控股材料厂商在A股上市，具备AI加双足及轮式人形机器人全栈能力，其资本运作规划带动合作零部件厂商股价底部异动；宇树科技公开表示年收入已突破10亿元，有望下半年加速上市；智元、宇树同时中标中国移动旗下接近1.2亿元人形机器人采购订单，有望部署在移动营业厅与消费者互动。
-- **对商业场景的判断**：优先关注投资回报率相对明确的场景，重点提示物流端——降低单件运输成本是2025年下游客户明确刚需；国内至少100家以上人形机器人本体厂商，需从投资角度布局。
-- **对特斯拉延期的解读**：Optimus存在电机过热、灵巧手负载不足、续航问题等硬件问题，特斯拉正在变更方案、筛选供应商；这些硬件瓶颈恰是发展人形机器人的共性瓶颈——无框力矩电机新品用于改善散热性能，轻量化（以塑代钢、替代铝合金）是解决续航的值得关注方向。
-- **对港股机器人板块的判断**：二季度港股机器人板块估值溢价明显（无论PE还是PS），来自流动性和企业进入港股通/港股指数后享受全球科技资金关注；下半年港股机器人板块有确定性扩容，可关注A+H动向。
-- **对三季度投资信号的判断**：三季度是从二季度迷茫期到商业兑现的过渡阶段，建议关注三类信号——华为云生态接入厂商三季度继续新增；头部企业出货量跨越年化500台或1000台背后的股价及供应商演绎机会；聚焦电机硬件优化对应的窗口期。历史经验表明技术创新、产业需求、工厂替代三重周期共振时孕育较好投资机会。
-**中金公司传媒行业首席分析师张雪琴**就游戏板块表态：
-## 游戏板块
-- **对政策环境的判断**：今年游戏行业最大变化是政策端友好度空前——去年《黑神话：悟空》爆火后游戏行业文化价值和经济价值得到广泛认可，政府支持力度达到空前高度；今年1月和3月国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门政策支持包（含中小微企业奖励、数字内容文化产业出海支持、IP方向等），给企业稳定军心、长周期运营提供帮助，短期推动多年压制的估值修复。
-- **对版号发放的判断**：从去年四季度以来版号发放每月保持良好节奏，今年已进化到每月同时发放国产和进口网络游戏版号；6月单月版号发放创新高——国产147个、进口11个、总计158个，为2018年以来单月最高水平；持续稳定的版号发放使版号不再是产品上线障碍，而是正常审批流程，对暑期档新品推出速度和供给侧丰富有帮助。
-- **对市场景气的判断**：版号停发时增速掉到零以下，2024年8月以来市场单月持续正增长；今年1–5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%。
-- **对产品周期的判断**：今年存在预期差——年初市场认为缺乏产品大作（腾讯、网易、米哈游均无特别重磅作品），但中型厂商亮眼新品成为A股、港股中型公司核心催化；吉比特5–6月上线的《仗剑传说》首月流水两个多亿，对其边际带动已足够强；巨人网络《超自然行动组》6月预估流水过亿，乐观年化约20亿元流水量级，对其利润提升可能已达50%以上；大厂缺少大体量产品时对中型厂商产品获客非常友好，国内大多数新游获客ROI非常OK。
-- **对估值与投资节奏的判断**：游戏板块TTM PE约30倍（2023年AI行情下到过45倍），2025年静态PE约20倍、明年更低；当前板块与两年前不同——游戏已定义在当前消费趋势下的悦己型消费领域，不受宏观经济影响（1–5月同比增长17%），政策环境完全改变，新品周期还在延续（网易、腾讯等新品更多落在明年大周期）；新品存在前期买量成本投入和流水递延确认的后置差异，今年上新品的利润更多滞后到明年兑现，为明年业绩确定性提供基础。
-- **对调整性质的判断**：近期调整是回调一下更健康、可以上车的状态，而非结束；在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击；建议关注新品市场表现、用户获取下载榜排名等领先指标（流水是领先指标，利润相对滞后）。
+中金宏观策略周会由策略组刘刚凯文主持，围绕大美丽法案、关税政策、港股流动性、反内卷光伏、人形机器人及游戏板块等热点展开分析，并给出配置建议。大美丽法案方面，刘刚凯文指出法案提高债务上限约5万亿美元，延长2017年减税法案并取消899条款，延长减税每年额外支出约3400亿美元，减少新能源补贴1.4万亿美元，关税收入每年约3000-4000亿美元可覆盖额外支出，赤字率维持5-6%。三季度财政部发债约1万亿美元，可能推高美债利率，参考2023年三季度利率从3.8%升至5%。美股纳斯达克从底部反弹35%，市场对去美元化担忧过度，信用周期框架下美国经济环比改善，中国面临高基数压力。结论是美股美债波动提供再配置机会，四季度美元可能小幅走强，美股可能反弹跑赢。关税方面，刘刚凯文总结四点信息：关税大概率实施以支撑收入，需维持一定税率，当前有效税率约10-12%；若8月1日关税回升，有效税率可能回到10-15%，极端情况18%；对华关税约40-50%，越南转口限制40%，需关注8月12日中美谈判；关税对通胀影响有限，年底通胀可能升至3.3-3.4%。结论是关税是谈判技巧，市场逐渐脱敏，对经济影响可控。港股流动性方面，刘刚凯文分析港股5月后微观流动性释放，HIBOR大幅下降，港币触及7.85，金管局可能小幅收紧流动性，三季度流动性供给不如二季度，港股指数在23000-24000区间震荡，上行受限。港股银行股溢价低于20%，短期透支，但长期仍有空间。结论是港股流动性边际收紧，但基本面强可对冲，建议在合适位置布局长期方向。反内卷光伏方面，公用事业风光首席分析师刘佳妮指出全球光伏新增装机从2020年130GW增至2024年530GW，未来两年增速回落至10%左右；2025年全球光伏需求预计650-700GW，电池产能为需求1.5倍，硅片组件2倍，硅料2.5倍；2022年以来产业链价格下跌70%-90%，硅片电池2023年四季度亏损，硅料组件2024年二季度亏损。反内卷政策升级：6月29日人民日报发声，7月1日中财委会议，7月3日工信部座谈会。硅料环节集中度高，成本差距大，整合最迫切；多晶硅期货价格触及40元/公斤，现货价格上周大幅上涨；光伏玻璃第二轮产能出清，计划7月降产30%，需出清约2万吨；头部一体化组件企业穿越周期能力强，技术变革如颗粒硅使用比例提升至50%。结论是反内卷政策有望夯实行业底部，硅料环节整合最迫切，技术变革助力企业穿越周期。人形机器人方面，机械军工分析师郭文秀指出二季度A股机器人板块下跌约9%，跑输机械设备12个百分点，特斯拉标签股回调30%-40%；特斯拉量产时间线推迟，叠加中美关税，降低风险偏好；华为发布盘古世界模型和CloudRobot平台，构建多模态生成、规划、执行三大能力；智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿元，两家中标中国移动1.2亿元采购订单；特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，变更方案。建议关注华为云生态接入、头部企业出货量跨越500台/1000台、电机硬件优化三类信号。结论是三季度是迷茫期到商业兑现的过渡阶段，建议关注华为链、本土企业技术闭环、特斯拉延期带来的硬件替代机会。游戏板块方面，传媒行业首席分析师张雪琴指出6月版号单月发放158个（国产147个，进口11个），为2018年以来单月最高；2025年1-5月游戏市场规模同比增长17%，手游同比增长20%；吉比特《仗剑传说》首月流水2亿多元，巨人网络《超自然行动组》6月流水过亿，年化约20亿元；游戏板块TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍；新品利润有滞后性，今年新品利润明年兑现。结论是游戏板块在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击。
 # Q&amp;A环节
-**1. 记者（人民日报 张宇）**：大美丽法案对美元流动性和美债利率的具体影响是什么？对港股流动性会带来怎样的冲击？
-**刘刚凯文**：大美丽法案短期在7-9月会有抽水效应，财政部需发债约1万亿美元，参考2023年三季度发债1万亿美元推高美债利率从3.8%升至5%，美元走强，美股小幅下跌4-5%。但这次期限溢价已处于2013年以来高位，利率抬升幅度可能到不了5%以上。供给确定增加，但需求端若强可对冲，不一定重演股债汇三杀。对港股而言，美元流动性收紧叠加港币触及7.85、金管局需回收流动性，三季度流动性供给不如二季度，边际上偏负面，但基本面强可盖过影响。
-**2. 记者（财新 李欣）**：关税谈判的最新进展如何？市场为何反应冷淡？
-**刘刚凯文**：关税大概率会做，因为需要支撑收入，每年关税收入约3000-4000亿可覆盖大美丽法案额外支出。需维持一定税率，当前有效税率约10-12%，极端情况回到18%，太高通胀受不了。威胁提高税率可能是谈判技巧，市场静观其变。新变化是时间拖后，相比4月2日对等关税水平大部分回落，除巴西外。加拿大、墨西哥、欧盟贸易占比高需谈妥，其他国家即便增加一倍也不影响有效税率。对华关税约40-50%，越南转口限制40%，需关注8月12日中美谈判进展。
-**3. 记者（上海证券报 王芳）**：光伏反内卷政策升级后，行业价格是否已见底？哪些环节最受益？
-**刘佳妮**：多晶硅期货价格已触及40元/公斤，现货价格上周大幅上涨，较前一周35元左右上浮比例较高，硅料市场呈现触底企稳态势。硅片报价上涨约10%，电池涨约两分钱，组件涨幅相对靠后约10%。硅料环节最易整合：集中度高、成本曲线陡峭、供需比超200%，头部尾部厂商现金成本差距大（颗粒硅28元/公斤，尾部厂商45元/公斤）。光伏玻璃第二轮产能出清，7月降产30%，需出清约2万吨方可修复供需平衡。头部一体化组件企业穿越周期能力强，可通过收现款再发货、占用上游账期获得正向经营现金流。
-**4. 记者（证券时报 陈晨）**：人形机器人板块三季度有哪些催化剂？特斯拉延期对产业链有何影响？
-**郭文秀**：三季度围绕三条主线：华为云生态开放、本土企业技术闭环、特斯拉延期带来的硬件替代窗口。华为发布盘古世界模型和CloudRobot平台，支持点云和视频双模态，构建多模态生成、规划、执行三大能力，明确不造机器人，以RTC方式开放。智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿，两家同时中标中国移动约1.2亿人形机器人采购订单。特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，正变更方案筛选供应商，这恰是行业共性瓶颈，关注电机散热、轻量化（以塑代钢）方向。建议关注三类信号：华为云生态接入厂商新增、头部企业出货量跨越年化500台或1000台、电机硬件优化窗口。
-**5. 记者（中国证券报 刘洋）**：游戏板块近期调整后，估值是否已具备配置价值？新品周期能否持续？
-**张雪琴**：游戏板块TTM PE约30倍，2025年静态PE约20倍，相比2023年AI行情45倍仍有空间。今年1-5月游戏市场规模同比增长17%，手游增长20%，6月版号单月发放158个（国产147个、进口11个），为2018年以来最高。新品周期在延续：吉比特《仗剑传说》首月流水2亿多，巨人网络《超自然行动组》6月流水过亿，中型厂商新品成为A股、港股核心催化。但新品利润有滞后性，今年上线产品利润更多在明年兑现，表观估值不便宜但明年业绩确定性提供支撑。建议关注新品市场表现、下载榜排名等领先指标，板块在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击。</t>
+**1. 记者（人民日报 张宇）**：大美丽法案对美元流动性、美股美债及港股流动性具体有何影响？
+**刘刚凯文**：大美丽法案提高债务上限约5万亿美元，延长2017年减税法案并取消899条款。延长减税每年额外支出约3400亿美元，减少新能源补贴1.4万亿美元，关税收入每年约3000-4000亿美元可覆盖额外支出，赤字率维持5-6%。三季度财政部发债约1万亿美元，可能推高美债利率，参考2023年三季度利率从3.8%升至5%。美股纳斯达克从底部反弹35%，市场对去美元化担忧过度。信用周期框架下美国经济环比改善，中国面临高基数压力。结论是美股美债波动提供再配置机会，四季度美元可能小幅走强，美股可能反弹跑赢。港股流动性边际收紧，但基本面强可对冲，建议在合适位置布局长期方向。
+**2. 记者（新华社 李明）**：关税政策后续走向及对通胀的影响如何？
+**刘刚凯文**：关税大概率实施以支撑收入，需维持一定税率，当前有效税率约10-12%；若8月1日关税回升，有效税率可能回到10-15%，极端情况18%；对华关税约40-50%，越南转口限制40%，需关注8月12日中美谈判；关税对通胀影响有限，年底通胀可能升至3.3-3.4%。结论是关税是谈判技巧，市场逐渐脱敏，对经济影响可控。
+**3. 记者（财新 王芳）**：反内卷政策对光伏行业各环节的影响及投资机会如何？
+**刘佳妮**：全球光伏新增装机从2020年130GW增至2024年530GW，未来两年增速回落至10%左右；2025年全球光伏需求预计650-700GW，电池产能为需求1.5倍，硅片组件2倍，硅料2.5倍；2022年以来产业链价格下跌70%-90%，硅片电池2023年四季度亏损，硅料组件2024年二季度亏损。反内卷政策升级：6月29日人民日报发声，7月1日中财委会议，7月3日工信部座谈会。硅料环节集中度高，成本差距大，整合最迫切；多晶硅期货价格触及40元/公斤，现货价格上周大幅上涨；光伏玻璃第二轮产能出清，计划7月降产30%，需出清约2万吨；头部一体化组件企业穿越周期能力强，技术变革如颗粒硅使用比例提升至50%。结论是反内卷政策有望夯实行业底部，硅料环节整合最迫切，技术变革助力企业穿越周期。
+**4. 记者（证券时报 陈晨）**：人形机器人行业三季度投资主线及催化剂有哪些？
+**郭文秀**：二季度A股机器人板块下跌约9%，跑输机械设备12个百分点，特斯拉标签股回调30%-40%；特斯拉量产时间线推迟，叠加中美关税，降低风险偏好；华为发布盘古世界模型和CloudRobot平台，构建多模态生成、规划、执行三大能力；智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿元，两家中标中国移动1.2亿元采购订单；特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，变更方案。建议关注华为云生态接入、头部企业出货量跨越500台/1000台、电机硬件优化三类信号。结论是三季度是迷茫期到商业兑现的过渡阶段，建议关注华为链、本土企业技术闭环、特斯拉延期带来的硬件替代机会。
+**5. 记者（上海证券报 刘洋）**：游戏板块估值水平及后续投资机会如何？
+**张雪琴**：6月版号单月发放158个（国产147个，进口11个），为2018年以来单月最高；2025年1-5月游戏市场规模同比增长17%，手游同比增长20%；吉比特《仗剑传说》首月流水2亿多元，巨人网络《超自然行动组》6月流水过亿，年化约20亿元；游戏板块TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍；新品利润有滞后性，今年新品利润明年兑现。结论是游戏板块在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>106.5</v>
+        <v>94.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22868/11306</t>
+          <t>22868/7329</t>
         </is>
       </c>
     </row>
@@ -3853,67 +3818,65 @@
       <c r="C10" t="inlineStr">
         <is>
           <t># 课程概况
-本节为以“梦想”为主题的班会课，由主讲老师主持。课程以师生互动开场，学生分享当保安、喜剧人、歌手等梦想，老师随后以自身经历为主线展开：高中立志考中国美术学院，单考已过但因离家远和家庭经济原因未入读，最终选择定向师范入读广东技术师范大学（原民族学院），毕业后回龙川县任教。老师回顾大学期间保持专业排名第一（专业共41人）、加入学生会、参加比赛、考取教师资格证等追梦历程，并强调实现梦想需坚持、努力、勇敢、机会、兴趣、能力与学习等条件。课程通过播放航模爱好者何宗发与普通歌手追梦的视频，组织“梦想观察团”游戏讨论实现梦想的条件，并以马云为例说明起点低可通过坚持成功。最后，老师引导学生写下个人梦想清单，分享部分学生梦想，建议先定小目标再逐步实现大目标，鼓励学生量力而行、坚持追梦。
+本节为以“梦想”为主题的班会课，由主讲老师主持。课程围绕梦想展开，老师先分享个人追梦经历：高中梦想考中国美术学院，单考通过但因离家远、家庭经济原因未就读，最终选择定向师范，入读广东技术师范大学（原民族学院），毕业后回龙川县教书；大学期间保持专业排名第一（专业共41人），并实现加入学生会、参加比赛、考取教师资格证等梦想。随后播放航模爱好者何宗发（音）与普通歌手追梦的视频，组织学生分组讨论实现梦想所需条件，结论为需要坚持、努力、勇敢、机会、兴趣、能力和学习，其中学习、坚持、行动是必不可少的三个条件。老师还以马云为例说明梦想可逐步立高，并强调每个梦想都值得尊重。最后让学生写下个人梦想清单，分享部分学生梦想并逐一点评鼓励，建议梦想可列清单、分阶段实现，先定小目标再定大目标。
 # 核心知识点梳理
 ## 梦想的定义与价值
-- **梦想的普遍性**：老师开场提问学生梦想，学生回答包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等，老师指出「每一个班的人都会有想当太空人」，说明广告词深入人心。
-- **梦想值得尊重**：老师强调「每一个梦想都是值得我们尊重的」，并以视频中唱歌走调的普通人为例，说明通过后天学习和努力可以调整，**不要去嘲笑任何一个人的梦想**。
-- **不被嘲笑的梦想**：老师引用「不被嘲笑的梦想不是梦想」，回忆自己在高中国旗下讲话时立志考中国美术学院，当时**底下很多人嘲笑**，但最终单考通过。
-- **梦想的独特性**：针对「马云梦想不可复制」的观点，老师指出**每一个人的梦想都是不可以复制的，都是独一无二的**。
+- **梦想的普遍性**：老师提问班级同学梦想，学生回答包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等，老师指出每个班都有人想当太空人，说明广告词深入人心。
+- **梦想值得尊重**：老师强调**每一个梦想都是值得我们尊重的**，不要嘲笑任何人的梦想，尽管他现在在睡觉也好，在干什么都好，顶峰相见。
+- **不被嘲笑的梦想**：老师引用「不被嘲笑的梦想就不是梦想」，并提到这是马云说的，鼓励学生有了梦想就要努力实现。
+- **梦想不可复制**：老师指出马云的成功是神话、不可复制，**我们每一个人的梦想都是不可以复制的，都是独一无二的**。
+## 老师的追梦经历
+- **高中梦想**：老师高中梦想考中国美术学院，单考已通过，并在国旗下讲话当着全校面宣布这一目标，当时**底下很多人嘲笑**。
+- **选择定向师范**：老师最终未就读中国美术学院，原因一是离家太远，二是家庭经济困难——学美术需要钱，老师高中靠大家资助一路成长；父母选择可定向回龙川县教书的学校，老师当时**哭了三天**，但现在很开心的，认为听了父母的选择是真的。
+- **大学就读**：老师入读广东技术师范大学（原民族学院，后改名广师大），定向生**免学费**，本科六年。
+- **大学梦想清单**：包括加入学生会、参加各种比赛（如校运会）、保持专业排名第一、考教师资格证；老师大学四年保持本专业排名第一，专业共41人。
+- **定向生限制**：⭐ 定向生**不能考研**，但可以**在职考研**——边工作边读研，学费自理。
+- **梦想之路时间线**：从读书开始到考上大学经历**11年**；录取优秀班干部用了**2年**（学校实行班团一体化，既做班长又做团支书）；获得国家励志奖学金用了**1年**；成为优秀人民教师的目标**还没开始、待定**。
 ## 实现梦想的条件
-- **坚持与努力**：老师指出实现梦想需要坚持和努力，并以马云为例——中考考了两次才考上高中、高考考了三次，最终成为中国首富，说明**起点高低不重要，关键看能否坚持**。
-- **勇敢与行动**：老师表扬班里同学在起哄中仍勇敢站上讲台唱歌，希望同学们都能有勇气去行动。
-- **机会留给有准备的人**：老师强调实现梦想需要机会，而**机会永远留给有准备的人**。
-- **兴趣、能力与学习**：老师指出兴趣、能力以及学习都是实现梦想的必备条件；缺少某一个条件梦想仍可能实现，但**条件都具备时梦想会更快实现**。
-- **学习、坚持、行动三要素**：老师小结时强调**学习、坚持、行动是梦想条件中必不可少的三个**。
-## 梦想观察团游戏
-- **游戏规则**：全班4个大组各为一个「梦想观察团」，观察对象是玩航模的小伙子和想成为歌手的普通人，讨论实现梦想需要具备哪些条件。
-- **航模案例**：视频中何宗发是中国唯一去法国巴黎比赛的航模选手，目标是「带着我的飞机环游世界各国，把中国国旗挂在世界各大赛场上」；他表演的飞机有真实原型机**歼10**，并计划在**明年世界锦标赛**再比高下。
-- **航模案例的成长**：何宗发因节目带动更多人参加航空模型行列，受到国内外模型爱好者甚至世界冠军关注，老师总结他通过一步步努力走上更大舞台，把航模事业做得**风生水起**。
-- **歌手案例**：视频中普通人在宿舍练习唱歌，即使天生嗓子走调，也可通过后天学习和努力调整过来，仍有可能成为歌手。
-## 老师的梦想之路
-- **当前梦想**：老师梦想成为**受学生喜爱的、有名望的优秀人民教师**，目前仍在努力过程中。
-- **高中梦想**：老师高中时立志考**中国美术学院**，单考已过，但因**离家远**和**家庭经济原因**（学美术费用高，老师高中靠大家资助成长）未去就读。
-- **大学选择**：老师选择定向师范，入读**广东技术师范大学**（原民族学院，后改名广师大），定向生**免学费**，毕业后回龙川县教书；老师当时为此**哭了三天**，但如今认为父母的选择是对的。
-- **大学成就**：老师大学期间保持**本专业排名第一**（专业共41人），每天**5点起床**，坚持自律；还实现加入学生会、参加比赛（如校运会）、考取**教师资格证**等梦想。
-- **定向生限制**：定向生**不能考研**，但可在职考研，需**边工作边读研**且**学费自费**。
-- **梦想之路时间线**：从读书到考大学经历**11年**；录取优秀班干部用了**2年**（学校实行班团一体化，班长兼团支书）；获得**国家励志奖学金**用了**1年**；成为优秀人民教师的目标**尚未开始，时间待定**。
-## 梦想清单的制定
-- **制定方法**：老师要求学生拿出纸写下梦想清单，像老师一样**列清单**：第1个是什么、第2个是什么，实现后**打勾**，并思考实现梦想需要的时间及实现后的收获。
-- **分阶段目标**：老师建议梦想可以一步步立高，如先定考进年级前百，实现后再定前50；梦想清单列得多，实现几率也更大，可先定**小目标**再定**大目标**。
-- **量力而行与调整**：老师小结指出，有梦想有追求会有困惑，需要**量力而行**，目标实现不了可以**调整目标**，通过努力坚持去实现。
-- **追梦的意义**：老师指出**追梦的人是特别充实的**，梦想或许坚持到底、也许会受挫折，但回头看时会明白当下为什么定下这些梦想。
+- **视频案例一（航模）**：航模爱好者何宗发（音）通过一步步努力走上更大舞台，是中国唯一去法国巴黎比赛的航模选手，梦想带着飞机环游世界各国、把中国国旗挂在世界各大赛场上，并计划参加明年世界锦标赛；他表演的飞机有真实原型机**歼10**，还去过中国航空博物馆学习原理。
+- **视频案例二（歌手）**：普通人想当歌手，在宿舍练习；有人天生天籁之音，有人唱歌走调会被嘲笑，但**走调通过后天学习和努力可以调整过来**，仍能成为歌手。
+- **必备条件**：实现梦想需要**坚持、努力、勇敢、机会、兴趣、能力、学习**；其中**学习、坚持、行动是必不可少的三个条件**。
+- **机会与准备**：机会永远留给**有准备的人**；缺少某一个条件梦想仍可能实现，但条件都具备时梦想会**更快速地实现**。
+- **梦想分阶段调整**：梦想可以一步步立高，如航模者从想在中国到想全世界；考不进年级前50可先调整为前百，考进前百再定前50，**先定小目标再定大目标**。
+## 学生梦想清单分享
+- **梦想清单写法**：老师建议学生用漂亮纸写下梦想，像老师一样列清单，逐条写第1个、第2个、第3个，实现后打勾，并思考实现梦想所需时间及实现后的收获。
+- **学生梦想示例一**：考试争取考到**630分**，同时拥有健康身体，希望每天开开心心、家人平平安安、世界和平、祖国越来越好。
+- **学生梦想示例二**：想改变打球动作、完成自定任务、成为设计师、大学四年攒**20万**、考上好大学、成为创业者并迎娶白富美。
+- **学生梦想示例三**：考试圆满通过、考上山西文化大学（音）、娶贤惠妻子、父母身体健康。
+- **学生梦想示例四**：不想成为流浪画家而要做画家、了解各国国家历史、多与同学拍照。
+- **学生梦想示例五**：想考师范大学、打羽毛球和篮球，成为一名光荣的人民教师。
+- **老师点评**：老师认为学生梦想「非常不错」「很朴实」，并说「我们要相信每一个同学的梦想都要相信他」；有学生只写了一个梦想，老师指出梦想可以制定多个，制定一个就要不断努力去实现。
 # 课堂互动与答疑
 **学生**：老师，定向生是不是就不能考研了？
-**教师**：定向生在校期间不能考研，但可以在职考研——边工作边读研，学费需自己承担。这是定向培养协议的限制，毕业后须按约定回定向地区任教。
-**学生**：老师，如果梦想实现不了怎么办？
-**教师**：梦想可以分阶段调整。比如想考进年级前50名，暂时达不到就先定前100名，实现后再逐步提高目标。量力而行、适时调整，通过坚持和努力逐步靠近大目标。
-**学生**：老师，唱歌走调的人也能实现歌手梦吗？
-**教师**：可以。唱歌走调可以通过后天学习和训练调整过来，天赋不是决定因素。实现梦想需要坚持、努力、勇敢、机会、兴趣、能力和学习，机会永远留给有准备的人。
-**学生**：老师，实现梦想需要具备哪些条件？
-**教师**：核心条件是学习、坚持和行动，三者缺一不可。此外还需要勇敢、机会、兴趣和能力。条件越充分，梦想实现越快；缺少某个条件，梦想仍有可能实现，但会受影响。
+**教师**：定向生不能在校全日制考研，但可以在职考研，边工作边读研，学费自理；这是定向协议的限制，毕业后须回龙川县教书。
+**学生**：老师，如果梦想定得太高实现不了怎么办？
+**教师**：梦想可以分阶段调整，先定小目标再定大目标，比如先考进年级前百，再逐步往前五十迈进；实现梦想需要坚持、努力、行动，这三个是必不可少的条件，机会留给有准备的人。
+**学生**：老师，唱歌走调的人还能实现当歌手的梦想吗？
+**教师**：可以，唱歌走调可以通过后天学习和努力调整过来，不要嘲笑任何人的梦想；天赋只是1%，坚持努力、勇敢行动才是关键。
+**学生**：老师，你大学是怎么保持专业排名第一的？
+**教师**：每天5点起床坚持学习，大学四年保持本专业41人中排名第一；自律和坚持是核心，同时积极参加比赛、加入学生会锻炼综合能力，评优不只看成绩。
 # 课后任务与学习建议
 ## 课堂练习
-- **梦想观察团游戏**：全班分4个大组，各为一观察团，观察对象为航模爱好者何宗发与想当歌手的普通人，讨论实现梦想需要具备的条件。
-- **梦想清单写作**：学生拿出纸张，仿照老师示例列出梦想清单，每项注明实现所需时间与实现后的收获，完成后由每组第1位同学收齐交给老师。
-- **梦想清单分享**：老师展示并点评部分学生梦想，如考630分、成为设计师、大学四年攒20万、成为人民教师等，引导学生体会梦想可大可小、可多可少。
+- **梦想条件讨论**：以航模爱好者何宗发（音）和想当歌手的普通人为观察对象，全班分4个大组组成“梦想观察团”，讨论实现梦想需要具备的条件，结论为坚持、努力、勇敢、机会、兴趣、能力和学习。
+- **梦想清单书写**：学生拿出纸写下自己的梦想，可仿照老师示例列清单，逐条写清梦想内容、预计实现时间及实现后的收获，写完后由每个小组第1个同学收集交给老师。
 ## 复习重点
-- **实现梦想的条件**：坚持、努力、勇敢、机会、兴趣、能力与学习，其中学习、坚持、行动是必不可少的三个条件；机会永远留给有准备的人。
-- **梦想可调整与分阶段**：目标实现不了可量力调整，如先定考进年级前百再冲前50；梦想可先定小目标再逐步实现大目标，梦想清单可列多项并逐项打勾。
-- **不嘲笑他人梦想**：唱歌走调可通过后天学习调整，不要嘲笑任何人的梦想，每个梦想都值得尊重；不被嘲笑的梦想不是梦想。
-- **起点高低不影响成功**：以马云中考两次、高考多次才考上为例，说明起点低可通过坚持取得成功；梦想不可复制，每个人独一无二。
+- **实现梦想的三大必要条件**：学习、坚持、行动，三者缺一不可；具备全部条件时梦想会更快实现。
+- **梦想可分阶段调整**：目标实现不了时可先调整为更易达成的阶段目标（如先考进年级前百再冲前50），一步步向前推进。
+- **每个梦想都值得尊重**：不被嘲笑的梦想不是梦想；不要嘲笑任何人的梦想，无论其当前状态如何。
+- **机会留给有准备的人**：实现梦想需要机会，但机会永远留给有准备的人，需以兴趣、能力和学习作支撑。
 ## 学习建议
-- **制定个人梦想清单**：仿照老师示例，列出短期与长期梦想，注明实现所需时间与收获，实现后打勾，建议先定小目标再逐步提高。
-- **坚持与行动**：老师以大学4年保持专业排名第一（专业41人）为例，说明需每天5点起床的自律与坚持；梦想需要付诸行动，勇敢站上舞台展示自己。
-- **调整目标量力而行**：梦想实现不了时及时调整目标，如考不进前50先定前百；定向生不能在校考研但可在职考研，需自费，选择路径要结合自身条件。</t>
+- **制定梦想清单**：仿照老师示例，将梦想分条列出（如考上理想学校、加入学生会、考取教师资格证等），实现一项打一个勾，并标注预计用时与收获。
+- **分阶段设定目标**：先定小目标再定大目标，梦想可以一步步立高（如航模爱好者从国内舞台走向世界锦标赛），量力而行并及时调整。
+- **勇敢行动**：像班会中主动上台唱歌的同学一样，即使被起哄也要勇敢站上讲台展示自己，用行动推动梦想实现。
+- **坚持与自律**：老师为保持专业排名第一坚持每天5点起床，说明实现梦想需长期坚持与自律，可借鉴此做法规划日常学习节奏。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>49</v>
+        <v>47.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9362/3323</t>
+          <t>9362/3129</t>
         </is>
       </c>
     </row>
@@ -4088,93 +4051,104 @@
       <c r="C11" t="inlineStr">
         <is>
           <t># 全文摘要
-本期新闻联播围绕国内发展成就与国际动态展开播报。国内方面，重点报道了文化自信与中华民族现代文明建设、赵乐际访俄、夏粮产量创历史新高、铁路货运增长、快递业提速、油气管网建设及渝川皖等地防汛应对等；国际方面，涉及多国人士评价中国改革、特朗普遇刺、加沙空袭、黎以冲突、俄乌冲突及加拿大林火等事件。文化领域，习近平总书记提出将中华优秀传统文化精华与马克思主义立场观点方法相结合，2023年10月首次提出习近平文化思想。赵乐际于7月9日至13日对俄罗斯进行正式友好访问，出席中俄议会合作委员会第九次会议，双方同意从立法机构层面落实两国元首共识。今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；6月份国家铁路发送货物3.32亿吨，同比增长6.1%；上半年快递业务量超800亿件；预计全年新增管道里程超4000公里。
+本期新闻联播由央视播音员播报，围绕国内发展成就与国际动态展开，涵盖文化自信与改革、赵乐际访俄、夏粮丰收、铁路货运、快递业、油气管网、防汛及国内联播快讯等主题。文化方面，习近平总书记提出将中华优秀传统文化精华与马克思主义立场观点方法相结合，2023年10月首次提出习近平文化思想；赵乐际于7月9日至13日访俄并出席中俄议会合作委员会第九次会议，双方同意从立法机构层面落实两国元首共识。国内经济数据方面发布了夏粮、货运、快递等多组创新高数据，其中夏粮产量达2996亿斤、6月铁路发送货物3.32亿吨、上半年快递业务量超800亿件；防汛方面，重庆等地出现暴雨，水利部联合调度水库应对三峡洪峰。国际方面，特朗普竞选集会遭未遂刺杀，以军空袭加沙致90人死亡。本期以信息发布为主，未形成明确结论。
 # 分段速览
 ## 00:00-08:31 文化自信与中华民族现代文明建设
-党的十八大以来，习近平总书记以重大理论创新指导文化实践，在“五位一体”总体布局中对文化建设作出战略部署，纵深推进文化体制改革。报道回顾了总书记在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地的考察论述，强调将中华优秀传统文化精华与马克思主义立场观点方法相结合。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，2023年10月首次提出习近平文化思想。文化领域供给侧结构性改革深入推进，文旅融合、非遗保护、公共文化服务体系等取得进展，我国成为图书、电视剧、动漫等领域生产大国。
-## 08:31-12:31 赵乐际访俄并出席中俄议会合作委员会第九次会议
-全国人大常委会委员长赵乐际应俄联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议。双方就落实两国元首共识、深化立法机构合作达成一致。普京表示俄中立法机构高水平合作有助于推进双边合作优先议题，沃洛金表示俄坚定恪守一个中国原则。访问期间，赵乐际向俄无名烈士墓敬献花圈。
+习近平总书记强调将中华优秀传统文化精华与马克思主义立场观点方法相结合，在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时提出系列重要论述。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述“两个结合”重大意义；2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。文化体制改革方面，《深化文化体制改革实施方案》是中央深改领导小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。文化领域供给侧结构性改革深入推进，文化旅游深度融合、非遗保护传承制度完善、公共文化服务体系健全，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”。
+## 08:31-12:31 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
+全国人大常委会委员长赵乐际应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。在圣彼得堡会见总统普京，转达习近平主席的亲切问候，强调今年是中俄建交75周年，两国新时代全面战略协作伙伴关系高水平、高质量发展；在莫斯科与马特维延科、沃洛金分别会谈，表示要以两国元首重要共识为指引，深化多层级、多领域、多渠道交流合作。10日出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作五点建议。访问期间向俄无名烈士墓敬献花圈。
 ## 12:39-14:21 夏粮产量创历史新高
-今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。主产区一、二等小麦占比普遍较高，小麦质量为近年来最好水平。
+今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，夏粮首战告捷为全年粮食丰收奠定坚实基础。
 ## 14:21-16:03 6月份国家铁路货运多项指标稳定增长
-国铁集团数据显示，6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高。分品类看，化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量、集装箱、商品汽车、冷链货物发送量等均创历史同期新高。多式联运快车已覆盖各省会城市，铁海快线班列覆盖全国主要港口。6月份中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
+国铁集团数据显示，6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，均创历史同期新高，我国铁路货运量、货运周转量等指标稳居世界首位。重点物资运输保障有力，化肥农药运量同比增长26.2%增幅最大，煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。境内运输网络更加完善，多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口。国际联运量质齐升，中欧班列6月累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
 ## 16:03-17:22 上半年我国快递业发展提速
-今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件。快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，国际运输能力稳步增强。多地启用、升级跨境仓，农村寄递网络覆盖范围逐渐扩大，每天超1亿件快递包裹在农村地区流动。5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。快递业不断丰富服务场景，实现与制造业的融合发展。
-## 17:22-19:12 油气管网建设提速“全国一张网”不断完善
-今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。到2025年将初步形成四大油气战略通道，建成“五纵五横”天然气干线管网。
+截至6月30日，今年我国快递业务量已达800亿件。快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，国际运输能力稳步增强；多地启用、升级跨境仓，农村寄递网络覆盖范围逐渐扩大。每天超1亿多件快递包裹在农村地区流动，5—6月生鲜商品进入销售旺季、电商促销拉动线上消费，快递日均业务量近5亿件。快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
+## 17:22-19:12 我国油气管网建设提速“全国一张网”不断完善
+今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。到2025年将初步形成东北、西北、西南及海上四大油气战略通道，建成“五纵五横”天然气干线管网。
 ## 19:12-20:40 渝川皖等地积极应对降雨天气
-重庆28个区县出现暴雨，其中13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江出现内涝、滑坡等险情，消防救援人员转移被困群众；安徽滁州全椒县加强巡堤，处置堤防渗漏和管涌。水利部针对“七下八上”防汛关键期逐流域安排防御。长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江部分地区出现内涝、滑坡等险情，消防救援人员转移被困群众；安徽滁州市全椒县加强巡堤，及时处置堤防渗漏和管涌。水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
 ## 20:40-23:38 国内联播快讯
-北京上半年计划新开工的320个市区重大项目已全部开工，总投资超4000亿元，聚焦现代化产业、基础设施、城市更新等领域。燕矶长江大桥北岸主塔封顶，主跨1860米，连接湖北鄂州和黄冈，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军。内蒙古第34届草原那达慕在锡林浩特开幕，持续到8月底。外交部、全国妇联主办的“中非儿童手拉手”活动在京启动，五国儿童代表将在北京、河南参观访问。
-## 23:38-30:07 国际新闻
-多国人士高度关注即将召开的党的二十届三中全会，表示中国全面深化改革、扩大开放为世界提供更广阔市场和发展机遇。美国前总统特朗普在宾夕法尼亚州竞选集会遭未遂刺杀，右耳中枪受伤，一名观众死亡、两名重伤，枪手被特勤局狙击手打死。以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等予以谴责。以军袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地。叙利亚大马士革遭空袭致1名政府军士兵死亡。
-俄军打击乌军列车点，乌军击退俄军17次进攻。加拿大纽芬兰与拉布拉多省林火蔓延，过火面积100平方公里，9600人被疏散。
+北京上半年320个市区重大项目全部开工，总投资超4000亿元，聚焦现代化产业、基础设施、城市更新等领域。燕矶长江大桥北岸主塔封顶，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军。内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底。外交部、全国妇联主办的“中非儿童手拉手”活动在中国儿童中心启动，纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。
+## 23:38-28:37 国际新闻
+多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放为世界提供更广阔的市场和发展机遇。美国前总统特朗普在宾夕法尼亚州巴特勒市竞选集会上遭未遂刺杀，右耳中枪受伤，一名观众死亡、两名受重伤，枪手为20岁左右宾夕法尼亚州男性，被特勤局狙击手打死，联邦调查局正展开调查。以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，内塔尼亚胡称目标是哈马斯下属武装派别领导人，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等也予以谴责。以军还袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地；叙利亚首都大马士革遭空袭致1名政府军士兵死亡、3人受伤。
+## 28:37-30:27 国际联播快讯与专题
+俄罗斯国防部称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向乌军军用火车停车点，摧毁20件装备；乌克兰武装部队总参谋部称击退俄军17次进攻。加拿大东北部纽芬兰与拉布拉多省林火蔓延，过火面积100平方公里，拉布拉多城9600人被疏散，全国正应对500多起活跃林火、超400起失控。《全面深化改革中国式现代化万千气象》专题聚焦上海、浙江坚定不移全面深化改革、扩大开放，在推进中国式现代化建设中走在前列。
 # 要点梳理
 ## 文化自信与中华民族现代文明建设
-- **理论创新**：习近平总书记提出将中华优秀传统文化精华与马克思主义立场、观点、方法相结合，强调“我们五千年的文明，我们要尊重，也要弘扬”。
-- **重要会议**：2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述“两个结合”尤其是“第二个结合”的重大意义；2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。
-- **考察足迹**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院凝望“实事求是”匾额，指出一定要把真理本土化；在三苏祠强调汲取治国理政理念和思维；在武夷山朱熹园提出以时代精神激活中华优秀传统文化生命力。
-- **改革方案**：《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署。
-- **文化成就**：我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
-- **文化工程**：深入实施中华文明探源工程，高标准推进国家文化公园建设，中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版。
+- **理论创新**：习近平总书记提出把中华优秀传统文化精华与马克思主义立场、观点、方法相结合，为建设社会主义文化强国指明方向
+- **考察足迹**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院凝望“实事求是”匾额，指出一定要把真理本土化；在三苏祠强调善于从中华优秀传统文化中汲取治国理政的理念和思维；在武夷山朱熹园提出以时代精神激活中华优秀传统文化的生命力
+- **重要会议**：2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述“两个结合”尤其是“第二个结合”的重大意义；2023年10月全国宣传思想文化工作会议首次提出习近平文化思想
+- **制度文件**：《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署
+- **文化成就**：我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高；深入实施中华文明探源工程，高标准推进国家文化公园建设，中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版
 ## 赵乐际访问俄罗斯
-- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。
-- **中俄关系定位**：今年是中俄建交75周年，在两国元首战略引领下，中俄新时代全面战略协作伙伴关系高水平、高质量发展。
-- **赵乐际表态**：中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献；在涉及彼此核心利益问题上坚定相互支持。
-- **普京表态**：俄中立法机构始终保持高水平合作，有助于在立法层面推进双边合作的优先议题；加强俄中议会合作委员会工作有利于两国交流经验、互学互鉴。
-- **马特维延科表态**：发展对华关系得到俄社会广泛认同和支持，两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流。
-- **沃洛金表态**：俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
-- **议会合作委员会第九次会议**：赵乐际10日出席并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作等五点建议。
-- **其他行程**：赵乐际在莫斯科向俄无名烈士墓敬献花圈。
+- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议
+- **会见普京**：赵乐际转达习近平主席亲切问候，表示今年是中俄建交75周年，在两国元首战略引领下中俄新时代全面战略协作伙伴关系高水平、高质量发展；中国全国人大愿从立法机构层面落实两国元首重要共识
+- **普京表态**：请赵乐际转达对习近平主席的亲切问候，称俄中立法机构始终保持高水平合作，加强议会合作委员会工作有利于两国交流经验、互学互鉴，促进立法、地方等各领域合作
+- **与马特维延科、沃洛金会谈**：赵乐际提出以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持；用好中俄议会合作委员会、双边友好小组等机制和平台，互学互鉴立法经验
+- **俄方表态**：马特维延科表示发展对华关系得到俄社会广泛认同和支持，要加强立法合作，推进地方立法机构、青年议员和人大代表交流；沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政
+- **议会合作委员会第九次会议**：赵乐际10日出席并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作团结壮大“全球南方”力量等五点建议
+- **其他行程**：访问期间赵乐际在莫斯科向俄无名烈士墓敬献花圈
 ## 夏粮产量创历史新高
-- **总产量**：今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。
-- **单产数据**：夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤；单产实现恢复性增长，是夏粮产量增加的主要原因。
-- **政策支撑**：中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金。
-- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高。
-## 6月份国家铁路货运指标
-- **总体数据**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
-- **重点物资**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高。
-- **运输网络**：连接内陆物流节点城市的多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口。
-- **国际联运**：6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
-## 上半年快递业发展
-- **业务总量**：上半年快递业务量超800亿件，截至6月30日已达800亿件。
-- **国际运输**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线。
-- **农村网络**：每天超1亿件快递包裹在农村地区流动；5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。
-- **融合发展**：快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
+- **总产量**：今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，克服多重自然灾害影响
+- **单产数据**：夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤；单产恢复性增长是产量增加的主要原因
+- **政策支撑**：中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金
+- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，得益于集成技术推广应用、科学防灾减灾、收割晾晒及时
+## 6月份国家铁路货运
+- **总体数据**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位
+- **重点物资**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高
+- **境内网络**：连接内陆物流节点城市的多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口
+- **国际联运**：6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%
+## 上半年快递业
+- **业务总量**：截至6月30日，今年我国快递业务量已达800亿件
+- **国际能力**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；多地启用、升级跨境仓
+- **农村网络**：每天超1亿多件快递包裹在农村地区流动，5—6月生鲜商品进入销售旺季、电商促销拉动线上消费，快递日均业务量近5亿件
+- **融合发展**：快递业不断丰富服务场景，拓展服务领域，实现与制造业融合发展
 ## 油气管网建设
-- **年度目标**：预计全年新增管道里程超4000公里，“全国一张网”不断完善。
-- **重点工程**：西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
-- **管网现状**：主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。
-- **2025年规划**：初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”的天然气干线管网。
-## 渝川皖等地应对降雨天气
-- **重庆**：28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝。
-- **四川**：内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。
-- **安徽**：多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌。
-- **防汛调度**：长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程；水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+- **总体目标**：预计全年新增管道里程超4000公里，“全国一张网”不断完善
+- **重点工程**：西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进
+- **管网能力**：主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米
+- **2025年规划**：初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网
+## 渝川皖等地应对降雨
+- **重庆**：7月13日8时至14日8时，九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨；组织工作人员连夜抢险排涝，保障道路畅通
+- **四川**：暴雨造成内江部分地区内涝、滑坡等险情，消防救援人员紧急出动转移被困群众
+- **安徽**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌
+- **水利部调度**：针对“七下八上”防汛关键期逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程；联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量
 ## 国内联播快讯
-- **北京重大项目**：上半年计划新开工的320个市区重大项目全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超4000亿元。
-- **燕矶长江大桥**：北岸主塔封顶，下一步转入主缆施工阶段；大桥连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
-- **环青海湖国际公路自行车赛**：第二十三届在海北州门源县收官，8天8个赛段，国内外22支车队154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
-- **内蒙古草原那达慕**：第34届在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
-- **“中非儿童手拉手”活动**：由外交部、全国妇联主办，在中国儿童中心启动；来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问。
+- **北京重大项目**：上半年计划新开工的320个市区重大项目全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超4000亿元
+- **燕矶长江大桥**：7月14日北岸主塔封顶，下一步转入主缆施工阶段；连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道
+- **环青海湖国际公路自行车赛**：第二十三届7月14日在海北州门源县落幕，8天8个赛段，国内外22支车队154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军
+- **草原那达慕**：内蒙古第34届7月14日在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动
+- **中非儿童手拉手**：7月14日由外交部、全国妇联主办，在中国儿童中心启动；纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问
 ## 国际新闻
-- **多国人士评价中国改革**：高度关注即将召开的党的二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为世界提供更广阔的市场和发展机遇。
-- **特朗普竞选集会遭枪击**：13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击，特朗普称右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众受重伤；枪手从集会现场外高处向演讲台开枪，所处屋顶距演讲台约180多米到270多米，开枪后被特勤局狙击手打死；美联邦调查局称特朗普遭未遂刺杀，枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明。
-- **以军空袭加沙马瓦西地区**：13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者中包括许多妇女和儿童；以总理内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马；哈马斯表示袭击使局势“严重升级”。
-- **巴勒斯坦及多国谴责**：巴勒斯坦总统阿巴斯发表声明谴责以军违反国际法；约旦、卡塔尔、埃及等发表声明予以谴责。
-- **加沙其他冲突**：以军13日在拉法、加沙城等地打击巴武装人员和军用设施；巴武装派别使用迫击炮、火箭弹等打击以军阵地和坦克。
-- **黎以冲突**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾；黎真主党武装打击了位于以色列北部的以军集结地和情报设施。
-- **叙利亚遭空袭**：14日凌晨大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
-- **俄乌冲突**：俄军使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌军称当天在前线与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
-- **加拿大林火**：东北部纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大正应对500多起活跃林火，其中超400起处于失控状态。</t>
+- **多国人士评价**：高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放在许多领域实现历史性变革，为世界提供更广阔的市场和发展机遇
+- **特朗普竞选集会枪击**：13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击，特朗普在社交媒体称右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众受重伤；枪手从集会现场外高处向演讲台“开了数枪”，所处屋顶距演讲台约180多米到270多米，开枪后被特勤局狙击手打死；美联邦调查局称特朗普遭未遂刺杀，枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明
+- **以军空袭加沙马瓦西地区**：13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者中包括许多妇女和儿童；内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马，今后将继续发动类似袭击；哈马斯表示袭击使局势“严重升级”
+- **各方谴责**：巴勒斯坦总统阿巴斯发表声明谴责以军违反国际法；约旦、卡塔尔、埃及等发表声明予以谴责
+- **加沙其他冲突**：以军13日在拉法、加沙城等地打击巴武装人员和军用设施；巴武装派别使用迫击炮、火箭弹等打击以军阵地和坦克
+- **以黎冲突**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾；黎真主党武装称打击了位于以色列北部的以军集结地和情报设施
+- **叙利亚遭空袭**：叙利亚军方7月14日称大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标
+- **俄乌冲突**：俄国防部称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌武装部队总参谋部称当天与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻
+- **加拿大林火**：13日纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大正应对500多起活跃林火，其中超400起处于失控状态
+## 结论与决定
+- **文化领域**：全党全国各族人民文化自信明显增强，全社会凝聚力和向心力极大提升；文化体制改革在正本清源、守正创新中取得历史性成就、发生历史性变革
+- **中俄关系**：双方同意从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作；俄方明确坚定恪守一个中国原则
+- **夏粮生产**：夏粮首战告捷，为全年粮食丰收奠定坚实基础
+- **铁路货运**：6月份多项指标创历史同期新高，铁路货运量、货运周转量等指标稳居世界首位
+## 行动项与分工
+- **水利部**：针对“七下八上”防汛关键期逐流域安排防御，联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量
+- **美联邦调查局**：对特朗普竞选集会枪击事件展开调查，枪手具体作案动机有待查明
+## 待确认与风险
+- **特朗普枪击案**：枪手为20岁左右男性、来自宾夕法尼亚州，具体作案动机还有待查明
+- **以军空袭**：内塔尼亚胡称今后将继续发动类似袭击，哈马斯表示袭击使局势“严重升级”
+- **加拿大林火**：火势迅速升级，已无法继续使用灭火飞机，超400起活跃林火处于失控状态</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>74.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7755/6456</t>
+          <t>7755/7574</t>
         </is>
       </c>
     </row>
@@ -4413,128 +4387,142 @@
       <c r="C12" t="inlineStr">
         <is>
           <t># 课程概况
-本课为初中物理光学复习课，主讲人系统讲解几何光学核心内容，覆盖光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用五大板块。课程从光源定义（自身能够发光的物体，分自然光源与人造光源）和光线概念（带箭头的直线，属物理模型）入手，确立光在均匀介质中沿直线传播的基本规律，并以三点一线、激光准直、小孔成像、日食月食、影子形成等实例佐证；随后介绍光速，真空中为3×10⁸米/秒，一秒钟绕地球赤道7圈半，水中约为真空中的3/4，玻璃中约为2/3。反射部分讲解反射定律（三线共面、分居两侧、反射角等于入射角），纠正垂直入射时入射角为0度的常见错误，并对比镜面反射与漫反射，指出生活中大多数反射为漫反射，两种反射均遵守反射定律。平面镜成像特点为正立、等大的虚像，实验需注意玻璃板垂直且薄；球面镜部分介绍凸面镜发散光线、凹面镜会聚光线及其应用，并提及凹面会聚可能造成光污染隐患。课堂通过例题巩固知识点，包括光速计算（激光从地球到月球距离3.75×10⁸米）、视力表虚像距离（5米）等。
+本课为初中物理光学复习课，系统复习几何光学核心知识，涵盖光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用。主讲人指出几何光学自古希腊时期即有研究，初中阶段主要学习直线传播、反射与折射规律。光的直线传播部分讲解光源（自然光源与人造光源）、光线（物理模型）概念，通过激光笔与烟雾实验、吸管弯折实验证明光在均匀介质中沿直线传播，并指出大气层不均匀会导致光线偏折；实例包括三点一线瞄准、激光准直、小孔成像、日食月食、影子形成，光在真空中速度为3×10⁸米/秒。光的反射定律强调三线共面、分居两侧、反射角等于入射角，法线为垂直镜面的辅助线，光垂直入射时入射角与反射角均为0度。镜面反射与漫反射对比中，黑板反光属镜面反射，电影银幕产生漫反射，雨后夜晚判断水潭位置及光路可逆性均有涉及。平面镜成像特点为正立、等大、虚像，实验用玻璃板代替平面镜便于确定像的位置，并讨论实验误差原因。球面镜部分介绍凸面镜发散光线、凹面镜会聚光线及其应用，并提及玻璃幕墙光污染隐患。
 # 核心知识点梳理
 ## 光的直线传播
-- **光源定义**：自身能够发光的物体，分为自然光源（如太阳、萤火虫）和人造光源（如火把、蜡烛、煤油灯、电灯）。
-- **光线概念**：用一条带有箭头的直线代表光线，是**物理模型**，并非真实存在。
-- **传播规律**：光在均匀介质中沿直线传播；大气层不均匀时光线发生偏折，导致日出时太阳看似跃出地平线、夜晚星星「眨眼睛」。
-- **三点一线实例**：步枪瞄准时眼睛、准心尖、标尺缺口三者重合即三点一线，依据是光在均匀介质中沿直线传播；队列排齐、木工闭眼检查尺子是否平直同理。
-- **激光准直**：利用激光沿直线传播的特性进行准直。
-- **小孔成像**：成**倒立实像**，放大缩小不一定，与孔形状无关；光线实际到达光屏故为实像；《墨经》有记载，是常考内容。
-- **小孔成像生活实例**：夏天大杨树下地面上的光斑是太阳透过树叶缝隙形成的小孔成像，因太阳距地球远大于树叶缝隙到地面距离，得到的是太阳**缩小**的像，角度不正时呈椭圆形。
-- **小孔成像自制实验**：纸杯底部用针扎小孔（不能用钉子扎大孔），杯口蒙塑料布，点燃蜡烛放在孔前方，可在塑料布上看到倒立的火苗像。
-- **日食形成**：太阳、月球、地球在同一直线上，**月球在中间**；1号区域为日全食，2、3号区域为日偏食，4号区域为日环食。
-- **月食形成**：太阳、地球、月球在同一直线上，**地球在中间**；月球完全进入1号区域为月全食，部分在1号区域、部分在2或3号区域时为月偏食；月球处于2、3号区域时仅略暗，不叫月偏食。
-- **影子形成**：影子（俗称阴影）的形成是光沿直线传播的实例，中国唐朝皮影戏即利用此原理。
-- **光在真空中的速度**：`3×10^8` 米/秒，即 `3×10^5` 千米/秒，约每秒30万公里，一秒钟绕地球赤道7圈半。
-- **光在其他介质中的速度**：空气中约 `2.99×10^8` 米/秒（比真空略慢，常近似处理）；水中约为真空中的 `3/4`；玻璃中约为真空中的 `2/3`。
-- **光速计算例题**：激光从地球射到月球表面用时1.25秒，按真空光速计算，距离为 `3.75×10^8` 米（`s=V×T`）。
-- **闪电与雷声**：先看到闪电后听到雷声，因为光速比声速快；声速在15℃时约340米/秒。
-- **易错点**：光沿直线传播必须强调**均匀介质**，只说「光沿直线传播」不严密；光在不同介质中传播速度不相同。
+- **光源定义**：自身能够发光的物体，分为**自然光源**（如太阳）和**人造光源**（如火把、蜡烛、煤油灯、电灯）。
+- **光线概念**：用一条带有箭头的直线代表光线，是**物理模型**，并非真实存在；按来源分为自然光源与人造光源，按形状分为点光源（如蜡烛）与平行光源（如太阳从无限远处来，画成一束平行光）。
+- **光沿直线传播条件**：光在**均匀介质**中沿直线传播；大气层不均匀时会发生偏折，如太阳越出地平线、夜晚星星眨眼。
+- **证明实验**：玻璃罩内用激光笔照射，借助熏香或烟雾显示光路；用吸管做实验——吸管弯折后，激光在墙上光点消失，说明光不会自行拐弯。
+- **实例——三点一线**：步枪瞄准时眼睛、准心尖、标尺缺口三者重合，依据是光在均匀介质中沿直线传播；队列排齐、木工师傅闭一只眼看尺子是否平直同理。
+- **实例——激光准直**：利用激光沿直线传播的特性进行准直。
+- **实例——小孔成像**：光沿直线传播，成**倒立实像**，放大缩小不一定，与孔形状无关；《墨经》有记载，考试常考。
+- **小孔成像生活案例**：夏天大杨树下地面上的光斑，是太阳透过树叶缝隙形成的小孔成像，因太阳距地球远大于缝隙距地面距离，得到的是**缩小的实像**，角度不正时呈椭圆形。
+- **小孔成像自制实验**：纸杯底部用针扎小孔，杯口蒙塑料布，点燃蜡烛放在孔前，可在塑料布上看到**倒立的火苗像**。
+- **实例——日食**：太阳、月球、地球在同一直线上，**月球在中间**；1号区域为**日全食**，2、3号区域为**日偏食**，4号区域为**日环食**。
+- **实例——月食**：太阳、地球、月球在同一直线上，**地球在中间**；月球完全进入1号区域为**月全食**；月球部分在1号区域、部分在2或3号区域时出现**月偏食**（仅处于2、3号区域只会略暗，不叫月偏食）。
+- **实例——影子形成**：影子即俗称的阴影，唐朝皮影戏利用此原理。
+- **光速**：光在真空中的传播速度为 `3×10^8` 米/秒，即 `3×10^5` 千米/秒，约**每秒绕地球赤道7圈半**；空气中略慢，近似取 `3×10^8` 米/秒；水中约为真空中的 `3/4`，玻璃中约为 `2/3`。
+- **介质含义**：此处介质指**透明**物质（如有机玻璃、水），砖头、黑板不算；海水清澈时太阳光最多到达约**200米**深处。
+- **光速测量**：前人测量光速均失败，初三将学习光本质为电磁波，电磁波速度即 `3×10^8` 米/秒。
+- **练习1**：影子和月全食均依据光在均匀介质中沿直线传播。
+- **练习2**：激光从地球射到月球表面用时1.25秒，距离 `s=V×T`，地球与月球间视为真空，答案 `3.75×10^8` 米。
+- **练习3**：先看到闪电后听到雷声，因为**光速比声速快**（声速15℃时约340米/秒）。
+- **练习4**：选C——光在均匀介质中沿直线传播；D错在未强调均匀介质。
+- **练习5**：多选，选BCD——平面镜是反射现象。
+- **练习6**：选ABC；D错在光说传播路线，须强调均匀介质。
 ## 光的反射定律
-- **基本概念**：入射光线 `AO`、入射点 `O`、反射光线 `OB`；法线 `OP` 垂直于镜面，是辅助线，**不是真实存在**，画虚线；入射角（角1）是入射光线与法线的夹角，反射角（角2）是反射光线与法线的夹角。
-- **反射定律三句话**：①反射光线、入射光线、法线在同一平面内（共面）；②反射光线和入射光线分居法线两侧；③反射角等于入射角。
-- **引入法线的目的**：为后续学习光的折射做准备，不能直接用入射光线与镜面的夹角代替入射角。
-- **易错点**：光垂直射到镜面上时，入射角和反射角均为 **0度**（不是90度），因为入射角是入射光线与法线的夹角。
-- **典型计算**：反射光线与平面镜夹角为40度时，入射角为50度（与法线夹角）。
-- **作图步骤**：①先画法线（虚线，画两三段即可，保留作图痕迹）；②根据反射角等于入射角画反射或入射光线；③补全箭头。可用刻度尺对称取点法（如法线对准20刻度，反射光上取25刻度点，入射侧对应取15刻度点）确定角度，无需量角器。
-- **常见作图错误**：箭头方向画反（两条光线各往各的方向飞）或相对而画。
-- **入射角变化规律**：入射光线与镜面夹角增大时，入射角减小，反射角也随之减小，传播速度不变。
+- **基本概念**：`AO` 为入射光线，`O` 为入射点，`OB` 为反射光线；`ON` 为**法线**，垂直于镜面，是入射光线与反射光线夹角的角平分线；入射光线与法线的夹角为**入射角**，反射光线与法线的夹角为**反射角**。
+- **反射定律三句话**：①反射光线、入射光线、法线在**同一平面内**（共面）；②反射光线和入射光线**分居法线两侧**；③**反射角等于入射角**。
+- **法线引入原因**：为后续学习折射做准备，法线是辅助线，**不存在**，画图用虚线。
+- **易错点**：光垂直射到镜面上时，入射角和反射角均为**0度**（不是90度）。
+- **例题——第9题**：反射光线与平面镜夹角40度，则与法线夹角50度，入射角为**50度**，选A。
+- **作图步骤**：①先画法线（虚线，画两三段断开即可，作图痕迹保留）；②根据反射角等于入射角，用刻度尺在法线两侧找对称点（如一侧5厘米，另一侧找5厘米）；③连接入射点与对称点，补全箭头。
+- **作图易错**：箭头方向画反（两条光线各往各的方向飞或相对着画），此类题定位为送分题。
+- **练习10**：入射光线与镜面夹角增大，入射角减小，反射角也减小，传播速度不变，选C。
+- **练习11**：入射光线与法线夹角60度，反射角为**60度**。
+- **练习12**：反射光线与入射光线夹角80度，反射角为**40度**（角平分线）。
 ## 镜面反射与漫反射
-- **镜面反射**：平行光射到光滑表面（如平面镜），反射光仍平行；人眼只有处在反射光线方向上才能看到，商场玻璃隔断易使人撞上即因此。
-- **漫反射**：平行光射到凹凸不平的表面，把每个小面看作小平面镜，反射光线射向各个方向；人眼在任何位置都能看到。
-- **生活应用**：生活中大多数反射是**漫反射**；黑板反光看不清粉笔字属于镜面反射，电影银幕、投影幕布、教室黑板表面粗糙是为了产生漫反射。
-- **共同规律**：镜面反射和漫反射**都遵守光的反射定律**。
-- **雨后水潭判断**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭。
-- **自制验证实验**：白纸上放一面小镜子，手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的——镜子发生镜面反射光线返回，白纸表面粗糙发生漫反射。
-- **光路可逆**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明在平面镜中的像，依据是光路可逆。
+- **镜面反射**：平行光射到光滑表面，各入射点法线均与镜面垂直，入射角相同，反射光平行射出；人眼只在特定位置能看到反射光，如商场玻璃隔断易使人撞上。
+- **漫反射**：表面凹凸不平，将每个小面看作小平面镜，平行光反射后射向**各个方向**，人眼在任何位置都能看到；生活中大多数反射是漫反射。
+- **黑板反光**：教室某些位置看黑板只见一片光亮、看不清粉笔字，是黑板发生**镜面反射**；电影银幕、投影幕布表面粗糙，发生**漫反射**。
+- **练习13（雨后水潭）**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭。
+- **自制实验**：白纸上放小镜子，手电筒垂直照射，斜着看时**镜子是黑的、白纸是亮的**——镜子发生镜面反射光返回，白纸发生漫反射。
+- **练习14（光路可逆）**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明，依据是**光路可逆**；A错（垂直入射反射角0度）、C错（漫反射也遵守反射定律）、D错（不同介质光速不同）。
+- **练习15**：电影院白色荧幕对光产生**漫反射**。
+- **练习16**：黑板反光为**镜面反射**，电影放映机射到银幕的光经幕布反射为**漫反射**，两种反射都遵守光的反射定律。
+- **练习17**：电影院白色屏幕粗糙，为使射到屏幕的光发生**漫反射**。
 ## 平面镜成像
-- **成像原理**：根据光的反射定律作图，反射光线反向延长线的交点即像点 `S'`；像与物的连线与镜面垂直，像到镜面距离等于物到镜面距离。
-- **成像特点**：成**正立、等大的虚像**；与小孔成像的倒立实像不同。
-- **实验器材与作用**：用玻璃板代替平面镜，便于移动后方蜡烛确定像的位置；刻度尺用于比较像与物到镜面的距离；两段完全相同的蜡烛用于比较像与物的大小。
-- **虚像验证**：光屏（毛玻璃、白塑料片、白墙等）不能接收到烛焰的像，因为实际光线没有到达镜后；后方蜡烛看似被点燃，手放上去不会被烫伤。
-- **实验误差原因一**：玻璃板与水平面不垂直（或与预先画好的镜面位置不重合），导致像与物到镜面距离测量不相等。
-- **实验误差原因二**：玻璃板有厚度，两个面都会发生反射成像；薄玻璃板（如3毫米）人眼分辨不出两个像，厚玻璃板（如8毫米）会看到同一个蜡烛的两个像。
-- **查视力应用**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子1.5米时看虚像距离为5米；若视力表距镜3米，人距镜2米即可。
-- **距离计算**：人站在平面镜前1米处，人与像之间的距离为2米；人向远离平面镜方向移动时，镜中像的大小**不变**。
-- **水中倒影辨析**：人在河边看到岸边的树在水中的倒影属于光的反射（平静水面充当平面镜），成的是正立等大的虚像，只是文学上习惯称「倒影」，易与折射混淆。
+- **成像原理**：根据光的反射定律作图，反射光线反向延长线的交点即像点 `S'`；像与物的连线**垂直于镜面**，像到镜面距离**等于**物到镜面距离。
+- **成像特点**：成**正立、等大、虚像**（与小孔成像的倒立实像不同）。
+- **实验器材与作用**：用**玻璃板**代替平面镜（便于移动后方蜡烛确定像的位置）；**刻度尺**用于比较像与物到镜面的距离；**两段完全相同蜡烛**用于比较像与物的大小。
+- **虚像验证**：光屏（毛玻璃、白塑料片、白墙等）**不能**接收到烛焰的像，因为实际光线没有到达镜后；后方蜡烛看似被点燃，手放上去不会被烫伤。
+- **实验误差原因一**：玻璃板与水平面**不垂直**（或与事先画好的镜面位置不重合），导致测量数据不相等。
+- **实验误差原因二**：玻璃板**有厚度**，两个面都发生反射成像；薄玻璃板（约3毫米）人眼分辨不出两个像，厚玻璃板（约8毫米）会看到同一个蜡烛的两个像。
+- **练习18**：人在河边看到岸边的树在水中的倒影属于光的反射（平静水面充当平面镜，成正立等大虚像，文学上称"倒影"）；C选项"看到河水深度比实际浅"是光的折射。
+- **练习21（查视力）**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子**1.5米**时看到虚像距离为5米。
+- **练习22**：视力表到镜距离改为3米，像到镜距离3米，人距镜子**2米**即可，选B。
+- **练习23**：人站在平面镜前1米处，人与像之间距离为**2米**。
+- **练习24**：人向远离平面镜方向移动，镜中像的大小**不变**，选C。
 ## 球面镜及其应用
-- **凸面镜**：对光线起**发散作用**，成**正立、缩小的虚像**；应用于汽车后视镜、丁字路口拐弯处反光镜；司机看后视镜感觉车距比实际远，即因凸面镜成像与真实有差异。
-- **凹面镜**：对光线起**会聚作用**，平行光反射后汇聚于焦点 `F`；应用于手电筒电珠（小灯泡置于焦点处）、汽车前大灯、探照灯、耳鼻喉科检查镜（中间镂空便于观察）、西藏藏民使用的太阳灶。
-- **凹面镜历史应用**：阿基米德曾组织妇女用梳妆镜（平面镜）围成凹面，汇聚光线烧毁敌人帆船。
-- **玻璃幕墙光污染**：玻璃幕墙做成凹面会汇聚光线，可能烧死树木（如学校枣树三年被烧死）、引燃焦点处的电线造成自燃，并反射声音造成噪音；设计师倾向用玻璃幕墙因其建筑成本高、设计费相应更高。
-- **作图方法**：球面镜作图采用「以直代曲」原则，把曲面看作许多小平面镜处理。
+- **凸面镜**：对光线起**发散作用**，成正立、缩小的虚像；用于汽车后视镜、丁字路口拐弯处反光镜（能看到更大范围，但视觉上物体显得比实际远）。
+- **凹面镜**：对光线起**会聚作用**，平行光反射后汇聚于焦点 `F`；用于手电筒电珠（小灯泡置于焦点处）、汽车前大灯、探照灯、医生额镜（中间镂空便于观察耳道、鼻腔、嗓子）、西藏藏民使用的太阳灶。
+- **作图方法**：以直代曲——将曲面看作许多小平面镜，逐面画法线与反射光线。
+- **阿基米德案例**：组织妇女用梳妆平面镜围成凹面，汇聚光线烧毁敌人帆船。
+- **玻璃幕墙光污染**：玻璃幕墙做成凹面会汇聚光线，可能烧死树木（学校枣树三年被烧死）、引燃电线（焦点落在电线上导致自燃）；凹面还反射声音，楼间噪音增大。
 # 课堂互动与答疑
 **学生**：为什么研究反射时要引入法线，直接用入射光线和镜面的夹角不行吗？
-**教师**：法线是为后续学习折射做准备的统一基准。若只用镜面夹角，折射定律将无法统一表述。法线是垂直于镜面的辅助线，实际不存在，画图时用虚线表示。
-**学生**：光垂直射到镜面上时，入射角和反射角是多少？
-**教师**：都是0度。入射角定义为入射光线与法线的夹角，垂直入射时二者重合，夹角为0度，反射角同样为0度。常见错误是答成90度。
-**学生**：为什么平面镜成像实验用玻璃板代替镜子？
-**教师**：玻璃板既能反射成像又能透光，便于在另一侧移动未点燃的蜡烛来确定像的位置。若用不透明镜子，无法观察到像的位置，实验无法进行。
-**学生**：实验中玻璃板有厚度，为什么能看到两个像？
-**教师**：玻璃板前后两个表面都能反射成像。薄玻璃板（约3毫米）两像几乎重合，肉眼难以区分；若用厚玻璃板（如8毫米），两像明显分离。实验应选用薄玻璃板。
-**学生**：为什么光屏接收不到平面镜所成的像？
-**教师**：平面镜成的是虚像，实际光线并未到达镜后，只是反射光线的反向延长线会聚形成的。因此光屏上无法接收到像，但人眼逆着反射光线方向看去能看到虚像。
-**学生**：为什么说平静水面的倒影是正立等大的虚像，却看起来是倒的？
-**教师**：水面相当于水平放置的平面镜，物体（如树）在镜中成的像相对物体本身是正立等大的。所谓"倒影"是文学描述，实际是物体相对水面的上下颠倒，与平面镜成像特点并不矛盾。
-**学生**：凸面镜和凹面镜对光线各起什么作用？
-**教师**：凸面镜对光线起发散作用，成缩小正立的虚像，用于汽车后视镜、丁字路口反光镜，视野更大。凹面镜对光线起会聚作用，焦点处可汇聚光线，用于手电筒、汽车前大灯、太阳灶、耳鼻喉科检查镜。
+**教师**：如果只研究反射，用镜面夹角确实可以，但后面还要学折射，折射定律需要以法线为基准来定义入射角和折射角，所以必须统一引入法线。法线是垂直于镜面的辅助线，也是入射光线和反射光线夹角的角平分线，实际并不存在，画图时用虚线表示。
+**学生**：光垂直射到镜面上，入射角和反射角是多少？为什么不是90度？
+**教师**：都是0度。因为入射角的定义是入射光线与法线的夹角，垂直入射时光线与法线重合，夹角为0度，反射角也等于0度。这是常见易错点，很多同学误答成90度。
+**学生**：画反射光线时，怎么确定入射光线的位置？需要用量角器量角度吗？
+**教师**：不需要量角器。作图步骤是：先画法线（虚线，留作图痕迹），再根据反射角等于入射角确定光线位置。简便方法是用刻度尺的刻度对准法线，在入射光线和反射光线方向上各找一个到法线距离相等的点，连接入射点即可，这样画出的两条光线一定对称。
+**学生**：为什么说小孔成像成的像一定是实像？放大缩小不一定？
+**教师**：因为光线实际到达光屏，所以是实像。像的大小取决于物距和像距的关系：物体离孔远、光屏离孔近时成缩小的像，反之成放大的像，但倒立是肯定的。像的形状与孔的形状无关，只与物体形状有关，如树叶缝隙形成的光斑是太阳的像。
+**学生**：日食和月食的偏食区域为什么不一样？月偏食不是月球在2、3号区域吗？
+**教师**：日食时月球在中间，2、3号区域是日偏食；但月食时地球在中间，月球很小，可以完全钻入地球阴影（1号区域）形成月全食。如果月球部分在1号区域、部分在2或3号区域，才出现月偏食；完全在2或3号区域时只是略暗，不叫月食。
+**学生**：光在真空中的速度是3×10⁸米/秒，那在其他介质中呢？
+**教师**：真空中是3×10⁸米/秒，空气中略慢，约为2.99×10⁸米/秒，通常近似取真空值；水中约为真空中的3/4，玻璃中约为2/3。光速随介质不同而变化，所以不能说光在所有介质中速度都相同。
+**学生**：为什么用玻璃板代替平面镜做成像实验？直接用镜子不行吗？
+**教师**：不行。平面镜不透光，无法看到镜后的蜡烛位置，也就无法确定像的位置。玻璃板既能反射成像，又能透过它看到后面的蜡烛，便于移动未点燃的蜡烛与像重合，从而确定像的位置并比较像与物的大小和距离。
+**学生**：实验中为什么能看到同一个蜡烛的两个像？
+**教师**：因为玻璃板有厚度，前后两个表面都能发生反射，各自成一个像。如果玻璃板很薄（如3毫米），两个像几乎重合，肉眼分辨不出；如果玻璃板较厚（如8毫米），就能明显看到两个像。所以实验应选薄玻璃板。
+**学生**：为什么光屏接收不到平面镜成的像？
+**教师**：因为平面镜成的是虚像，实际光线并没有到达镜后，只是人眼逆着反射光线的方向看过去，感觉像在镜后。所以把光屏放在像的位置，接收不到任何光线，也就看不到像。这与小孔成像不同，小孔成像是实际光线到达光屏形成的实像。
+**学生**：雨后夜晚，为什么迎着月光走时发亮处是水潭，背着月光走时发暗处是水潭？
+**教师**：水面发生镜面反射。迎着月光走时，月光经水面反射后恰好进入人眼，所以水潭发亮；背着月光走时，反射光射向另一侧，进入人眼的反射光很少，而地面发生漫反射，反而比水面亮，所以发暗处是水潭。
+**学生**：凸面镜和凹面镜对光线各起什么作用？分别用在哪些地方？
+**教师**：凸面镜对光线起发散作用，成**正立、缩小的虚像**，用于汽车后视镜、丁字路口反光镜，能扩大视野；凹面镜对光线起会聚作用，把平行光会聚到焦点，用于手电筒、汽车前大灯、太阳灶、医生额镜。凹面镜会聚光线也可能造成危害，如玻璃幕墙形成凹面会聚阳光，可能烧死树木甚至引燃电线。
 # 课后任务与学习建议
 ## 课堂练习
-- **练习1–5（直线传播）**：第1题考查光在均匀介质中沿直线传播；第2题影子和月全食均依据此原理；第3题激光从地球到月球用时1.25秒，按真空光速3×10⁸米/秒计算，距离为3.75×10⁸米；第4题选C（光在均匀介质中沿直线传播，B未说真空、D速度不相同）；第5题多选BCD（平面镜成像属反射，不选）。
-- **练习6（直线传播）**：多选选ABC；D错在未强调均匀介质，光传播路线并非无条件直线。
-- **练习7（反射定律探究）**：用带刻度硬纸板（中间用透明胶带粘合可前后转动）＋小平面镜＋激光笔，验证三线共面、分居两侧、反射角等于入射角。
-- **练习8（反射作图）**：先画法线（虚线，两三段即可），再根据反射角等于入射角画对应光线；可用尺子刻度对称找点（如法线对20刻度，反射光上找25，入射侧找15），保留法线痕迹、补全箭头。
-- **练习9（反射角计算）**：反射光线与平面镜夹角40°，则与法线夹角50°，入射角＝反射角＝50°，选A。
-- **练习10（入射角变化）**：入射光线与镜面夹角增大时，入射角减小、反射角也减小，传播速度不变，选C。
-- **练习11（反射角）**：入射光线与法线夹角60°时，反射角为60°。
-- **练习12（反射角计算）**：反射光线与入射光线夹角80°，反射角为40°（角平分线）。
-- **练习13（雨后水潭判断）**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭；选对应组合。
-- **练习14（光路可逆）**：A错（垂直入射反射角为0°）；B对（小明能看到小刚的像，则小刚也一定能看到小明的像，依据光路可逆）；C错（漫反射也遵守反射定律）；D错（不同介质光速不同）。
-- **练习15（漫反射）**：电影院白色银幕对光产生漫反射，选B。
-- **练习16（反射类型判断）**：黑板反光看不清粉笔字是镜面反射；电影银幕反射进入人眼是漫反射；两种反射都遵守光的反射定律。
-- **练习17（银幕粗糙目的）**：白色屏幕粗糙是为了使射到屏幕上的光发生漫反射。
-- **练习18（反射现象判断）**：人在河边看到岸边树在水中的倒影属光的反射（平静水面充当平面镜），选D；A、B为直线传播，C为折射。
-- **练习19（平面镜成像实验）**：记录数据中蜡烛到玻璃板距离与像到玻璃板距离不相等，原因是玻璃板与水平面不垂直（或未与预先画好的镜面位置重合）；同一侧看到两个像，原因是玻璃板有厚度，两个面发生反射成像。
-- **练习20（平面镜成像实验）**：用玻璃板代替平面镜是为了便于确定像的位置；刻度尺用于比较像与物到镜面的距离；两段完全相同蜡烛用于比较像与物大小；光屏不能接收到烛焰的像（虚像，实际光线未到达）；物体靠近玻璃板时像的大小不变。
-- **练习21（视力表）**：视力表距镜子3.5米，像距镜子3.5米，人距镜子1.5米时看虚像距离为5米，填1.5米。
-- **练习22（视力表）**：视力表到镜距离改为3米，像到镜距离3米，人到镜子2米即可，选B。
-- **练习23（平面镜距离）**：人站在平面镜前1米处，人与像之间距离为2米。
-- **练习24（平面镜大小）**：人向远离平面镜方向移动，像的大小不变，选C。
+- **第1–5题（光的直线传播）**：考点为光在均匀介质中沿直线传播及光速计算。第1题答案即该原理；第2题影子和月全食均依据此原理；第3题激光从地球到月球用时1.25秒，按s=vt计算，地月距离为3.75×10⁸米；第4题选C，光在真空中传播速度最快，均匀介质中沿直线传播，不同介质中速度不同；第5题多选BCD，平面镜成像属反射而非直线传播。
+- **第6题（多选）**：考点为光沿直线传播的条件，选ABC；D项错在未强调均匀介质，光传播路线并非无条件为直线。
+- **第7题（反射定律探究实验）**：考点为光的反射定律验证。用带刻度硬纸板（中间用透明胶带粘合可前后转动）和小平面镜，激光笔照射，观察反射光线、入射光线与法线关系，验证三线共面、分居两侧、反射角等于入射角。
+- **第8题（反射作图）**：考点为根据反射定律画入射或反射光线。步骤：先画法线（虚线，2–3段即可），再根据反射角等于入射角确定光线方向，最后补全箭头；可用尺子刻度找对称点辅助作图，作图痕迹保留法线即可。
+- **第9题（选择题）**：考点为入射角与反射角计算。反射光线与平面镜夹角40°，则与法线夹角（入射角）为50°，反射角也为50°，选A。
+- **第10题（选择题）**：考点为入射角变化对反射角的影响。入射光线与镜面夹角增大时，入射角减小，反射角随之减小，但传播速度不变，选C。
+- **第11题**：入射光线与法线夹角60°时，反射角为60°。
+- **第12题**：反射光线与入射光线夹角80°时，反射角为40°（角平分线）。
+- **第13题（雨后水潭判断）**：考点为镜面反射与漫反射辨析。迎着月光走，发亮处是水潭（水面镜面反射）；背着月光走，发暗处是水潭；选B。
+- **第14题（光路可逆）**：A错，垂直入射时入射角为0°而非90°；B对，小明能看到小刚在平面镜中的像，则小刚也一定能看到小明（光路可逆）；C错，漫反射同样遵守反射定律；D错，光在不同介质中速度不同。
+- **第15题**：电影院白色荧幕对光产生漫反射，选B。
+- **第16题（填空）**：教室某些位置看黑板只见光亮看不清粉笔字，是黑板发生镜面反射；电影放映机射到银幕的光经幕布反射进入人眼，是漫反射；两种反射都遵守光的反射定律。
+- **第17题**：电影院白色屏幕粗糙，为使射到屏幕上的光发生漫反射。
+- **第18题（选择题）**：下列现象属于光的反射的是D——人在河边看到岸边树在水中的倒影（平静水面充当平面镜）；A、B属直线传播，C属折射。
+- **第19题（平面镜成像实验）**：考点为实验误差分析。①蜡烛到玻璃板距离与像到玻璃板距离不相等，原因可能是玻璃板与水平面不垂直（或与事先画好的镜面位置未重合）；②同一侧看到同一个蜡烛的两个像，原因是玻璃板有厚度，两个面发生反射成像。
+- **第20题（平面镜成像实验）**：①用玻璃板代替平面镜的目的是便于确定像的位置（可透过玻璃板移动后方蜡烛找像）；②刻度尺用于比较像与物到镜面的距离；③两段完全相同蜡烛用于比较像与物的大小；④光屏不能接收到烛焰的像，因为平面镜成虚像，实际光线未到达后方；⑤物体靠近玻璃板时，像的大小不变。
+- **第21题（填空）**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子1.5米时，看到虚像距离为5米，填1.5米。
+- **第22题（选择题）**：视力表到镜距离改为3米，像到镜距离也是3米，人距镜子2米即可，选B。
+- **第23题**：人站在平面镜前1米处，人与像之间距离为2米。
+- **第24题**：人向远离平面镜方向移动，镜中像的大小不变，选C。
 ## 复习重点
-- **光源**：自身能够发光的物体；按来源分自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
-- **光线**：带有箭头的直线，是物理模型，并非真实存在；按形状分点光源（蜡烛）和平行光源（太阳，画平行光）。
-- **光沿直线传播**：光在均匀介质中沿直线传播；大气层不均匀时光线发生偏折（日出时太阳似越出地平线、星星眨眼）。
-- **直线传播实例**：三点一线（步枪瞄准、队列排齐、木工看尺子）、激光准直、小孔成像、日食月食、影子形成（皮影戏）。
-- **小孔成像**：成倒立实像（光线实际到达），放大缩小不一定，与孔形状无关；树下光斑是太阳通过树叶缝隙的小孔成像，为缩小的实像。
-- **日食与月食**：日食时太阳、月球、地球在同一直线，月球在中间，1号区域日全食、2/3号区域日偏食、4号区域日环食；月食时地球在中间，月球完全在1号区域为月全食，部分在1号区域、部分在2/3号区域才出现月偏食（仅处2/3号区域只是略暗，不叫月偏食）。
-- **光速**：真空中3×10⁸米/秒（3×10⁵千米/秒，约每秒30万公里，一秒钟绕地球赤道7圈半）；空气中约2.99×10⁸米/秒（近似取真空值）；水中约为真空中的3/4，玻璃中约为2/3；光速本质是电磁波速度。
-- **光的反射定律**：反射光线、入射光线和法线在同一平面内（三线共面）；反射光线和入射光线分居法线两侧；反射角等于入射角；法线垂直于镜面，是入射光线与反射光线夹角的角平分线，为辅助线（虚线，不存在）。
-- **垂直入射**：光垂直射到镜面上时，入射角和反射角均为0°（常见错误答成90°）。
-- **反射作图**：先画法线，再根据反射角等于入射角画入射或反射光线，保留法线作图痕迹，补全箭头。
-- **镜面反射**：平行光射到光滑表面，反射光平行，人眼在特定位置才能看到；商场玻璃隔断易使人撞上。
-- **漫反射**：平行光射到凹凸不平表面，反射光射向各个方向，人眼在任何位置都能看到；生活中大多数反射是漫反射（黑板、电影银幕、投影幕布、人眼看到物体）；两种反射都遵守光的反射定律。
-- **光路可逆**：在反射现象中光路可逆（小明能看到小刚在平面镜中的像，则小刚也一定能看到小明的像）。
-- **平面镜成像特点**：正立、等大的虚像；像与物到镜面距离相等，连线与镜面垂直；虚像不能用光屏接收（实际光线未到达）。
-- **平面镜成像实验**：用玻璃板代替平面镜（便于确定像的位置）；刻度尺比较像与物到镜面的距离；两段相同蜡烛比较像与物大小；玻璃板需与水平面垂直且选薄板（厚板两个面反射成两个像）。
-- **球面镜**：凸面镜对光线起发散作用，成正立缩小的虚像（汽车后视镜、丁字路口反光镜）；凹面镜对光线起会聚作用（手电筒电珠在焦点、汽车前大灯、探照灯、太阳灶、耳鼻喉科检查镜）；凹面镜会聚可致光污染（玻璃幕墙烧死树木、引燃电线）。
+- **光源**：自身能够发光的物体；按来源分为自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
+- **光线**：用带箭头的直线表示，是物理模型，并非真实存在；按形状可分为点光源（如蜡烛）和平行光源（如太阳光）。
+- **光在均匀介质中沿直线传播**：适用条件为同种均匀介质；大气层不均匀时光线发生偏折，表现为太阳越出地平线、星星眨眼等现象。
+- **光速**：真空中为3×10⁸米/秒（约每秒绕地球赤道7圈半）；空气中略慢（约2.99×10⁸米/秒）；水中约为真空的3/4；玻璃中约为真空的2/3。
+- **光的反射定律**：反射光线、入射光线和法线在同一平面内；反射光线和入射光线分居法线两侧；反射角等于入射角；法线垂直于镜面，是入射光线与反射光线夹角的角平分线。
+- **入射角与反射角**：均为光线与法线的夹角；光垂直射到镜面时，入射角和反射角都是0°（易错点：误答90°）。
+- **镜面反射**：平行光射到光滑表面，反射光平行，人眼在特定位置才能看到；黑板反光、平静水面倒影属此类。
+- **漫反射**：平行光射到凹凸不平表面，反射光射向各个方向，人眼在任何位置都能看到；电影银幕、白纸属此类；镜面反射和漫反射都遵守光的反射定律。
+- **光路可逆**：若甲能看到乙在平面镜中的像，则乙也一定能看到甲在平面镜中的像。
+- **平面镜成像特点**：正立、等大、虚像；像与物到镜面距离相等，连线与镜面垂直；虚像无法用光屏接收（实际光线未到达）。
+- **凸面镜**：对光线起发散作用，成正立、缩小的虚像；用于汽车后视镜、丁字路口反光镜。
+- **凹面镜**：对光线起会聚作用，焦点处可汇聚光线；用于手电筒、汽车前大灯、太阳灶、医生额镜；玻璃幕墙形成凹面会聚光线可能造成光污染。
 ## 学习建议
-- **自制小孔成像实验**：用纸杯底部拿针扎一个小孔（不要用钉子杵大孔），杯口蒙上塑料布，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像，体会像与孔形状无关。
-- **自制反射定律实验**：用硬纸壳（中间用透明胶带粘合可前后转动）画上均匀刻度格，搁一小平面镜，用激光笔照射，在家即可验证反射定律。
-- **自制镜面/漫反射对比实验**：白纸上放一面小镜子，用手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的（镜面反射光回去了，白纸漫反射光进入人眼）。
-- **购买激光笔**：两元店或十元店即可买到，激光强度大、光线直，适合研究直线传播和反射实验；也可用吸管验证光沿直线传播（直吸管激光能通过，弯折后墙上光点消失）。
-- **观察生活现象**：夏天到大杨树下看光斑（太阳通过树叶缝隙的小孔成像，缩小的实像，常为椭圆形）；雨后夜晚判断水潭位置（迎着月光走亮处是水潭，背着月光走暗处是水潭）。
-- **作图规范**：法线画虚线（两三段断开即可，不必画得太碎）；作图痕迹保留法线，补全箭头；用尺子刻度对称找点（如法线对20刻度，反射光上找25，入射侧找15）可快速画出对称光线。
-- **保护眼睛**：老师提醒长时间盯屏幕、写字姿势歪、教室整天拉窗帘不晒太阳都会导致视力下降；课间多到户外看远处，避免眼睛过度疲劳。</t>
+- **自制小孔成像实验**：用纸杯底部用针扎小孔（勿用钉子扎大孔），杯口蒙塑料布，点燃蜡烛置于小孔前方，可在塑料布上看到倒立的火苗像；体会像与孔形状无关。
+- **自制反射定律探究装置**：用硬纸壳（中间用透明胶带粘合可前后转动）、小平面镜和激光笔，在纸壳上画好刻度，即可在家验证光的反射定律。
+- **自制平面镜成像实验**：白纸上立一块透明玻璃，前方点燃蜡烛，后方移动未点燃蜡烛至像的位置，记录两蜡烛位置，可验证像与物到镜面距离相等、连线与镜面垂直。
+- **雨后水潭判断实验**：白纸上放一面小镜子，用手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的，直观理解镜面反射与漫反射的区别。
+- **购买激光笔**：两元店或十元店即可买到，激光笔光线强度大、线直，便于观察直线传播和反射实验，不必买昂贵型号。
+- **保护视力提醒**：主讲人强调长时间用眼、教室拉窗帘、写字姿势不良等都会导致近视；建议多到户外活动，避免长时间盯屏幕，注意用眼卫生。</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>78</v>
+        <v>82.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25691/7408</t>
+          <t>25691/8398</t>
         </is>
       </c>
     </row>
@@ -4645,124 +4633,135 @@
       <c r="C13" t="inlineStr">
         <is>
           <t># 课程概况
-电气工程基础是电气类专业进入专业课后的第一门入门课，由主讲人讲授。课程教学目的有二：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与整体的关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行、管理方面的基础理论、基本技术与计算方法。前修课程要求了解电路理论和电机学知识，特别是变压器和同步电机；后续重要课程包括电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。本次课程重点讲授第1章电力系统基本概念，包括基本概念、电力系统特点及要求、电能质量指标（含国家标准）、常用接地方式（重点为中心点接地方式），并梳理了交直流输电发展史、三相交流输电优势、电力系统形成过程与定义，以及电网和变电站的分类方法。
+电气工程基础是电气工程及其自动化专业的入门课程，本次为课程导论及第一章绪论部分。课程提出两个教学目标：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及其与电力系统整体的关系，建立电力系统的整体概念；二是掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术与计算方法。课程要求前修电路理论和电机学知识，特别是变压器和同步电机相关内容；后续重要课程包括电力系统分析、电力系统机电保护、电力系统自动化和高电压技术。本次课程主要内容包括：梳理交直流输电发展简史及交直流之争，论证三相交流输电的优势；从单机供电可靠性差出发，推导电力系统形成过程，给出电力系统、电力网、动力系统的定义；按规模将电网分为地方、区域、超高压远距离输送三类，并介绍变电站按电压等级和功率流向的分类方法。第一章为全课程概念最多、最重要的章节，重点掌握基本概念、电力系统特点与要求、电能质量指标及常用接地方式，难点在于有功无功动态平衡、额定电压规定和中心点接地方式。
 # 核心知识点梳理
-## 课程定位与学习目标
-- **课程性质**：电气工程基础是进入专业课后的**第一门课**，属于专业入门课，对今后工作非常重要。
+## 课程目标与定位
+- **课程定位**：电气工程基础是进入专业课后的**第一门课**，属于专业入门课，对今后工作非常重要。
 - **教学目标一**：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与电力系统整体之间的关系，建立电力系统的整体概念。
 - **教学目标二**：掌握电力系统在**分析、设计、运行、管理**方面的基础理论、基本技术及基本计算方法。
-- **前修课程**：要求对电路理论和电机学有一定了解，特别是**变压器和同步电机**知识要求较高；有欠缺的同学需自行补充相关内容。
-- **后续课程**：最重要的四门为电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。
+- **前修课程要求**：需了解电路理论和电机学知识，特别是**变压器和同步电机**相关知识要求较高；有欠缺的同学应课后补充相关内容。
+- **重要后续课程**：电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。
 ## 第1章学习内容与难点
-- **基本概念**：学习电力系统、电力网、动力系统和变电站等基本概念。
-- **电力系统特点与要求**：理解电力系统的特点及由特点引起的设计运行基础理论，理解对电力系统提出的要求。
-- **电能质量指标**：掌握电能质量指标及**国家标准**规定的各种范围。
-- **接地方式**：了解电力系统常用接地方式，重点是工作接地（中心点接地方式）的不同特点。
-- **难点一 ⭐**：电能不能大量储存，决定了电力系统**有功功率和无功功率的动态平衡**问题，是运行调整和设计的基础。
-- **难点二 ⭐**：电力系统额定电压的规定繁杂，需把额定电压规定搞清楚。
-- **难点三 ⭐**：各种中心点接地方式直接影响后续多个章节内容，学习较困难。
-- **学习方法**：注意概念的内涵和外延并适当记忆；从电力系统特点要求出发、从最基础原理推导，**不要记结论**（使用条件变化时结论将失效）；寻找额定电压规定之间的基本规律；比较不同中心点接地方式的特点。
+- **学习内容一**：掌握电力系统若干基本概念，包括电力系统、电力网、动力系统和变电站等相关概念。
+- **学习内容二**：理解电力系统的特点，以及由特点引起的电力系统设计、运行等方面的基础理论。
+- **学习内容三**：理解对电力系统提出的要求，涉及电力系统运行、设计和维护各方面。
+- **学习内容四**：掌握电力系统电能质量指标，包括**国家标准**对这些指标的各种规定范围。
+- **学习内容五**：了解电力系统常用接地方式，特别是**工作接地（中性点接地方式）**的不同特点。
+- **难点一** ⭐：由电力系统特点引出的基本原理，如**电能不能大量储存**决定了电力系统**有功功率和无功功率的动态平衡**问题，是运行调整和设计的基础。
+- **难点二** ⭐：电力系统**额定电压的规定**繁杂，需注意把规定搞清楚。
+- **难点三** ⭐：各种**中性点接地方式**直接影响后续多个章节内容，学习起来较困难。
+- **学习方法一**：对基本概念注意其**内涵和外延**，并适当记忆。
+- **学习方法二**：从电力系统特点和要求出发，**从最基础原理推导**，不要死记结论（结论在使用条件变化时会失效）。
+- **学习方法三**：注意寻找额定电压规定之间的**基本规律**。
+- **学习方法四**：注意**比较不同中性点接地方式**之间的特点。
 ## 直流输电发展简史
-- **早期试验**：福泰勒用2000米导线连接瓦斯发电机，拖动直流电动机和水泵，证明直流远距离输电可行。
-- **1874年**：俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率**4.5千瓦**。
-- **1882年**：法国德普勒架设首条**57公里**直流试验线路，首端电压343伏、末端850伏，输送功率200瓦，**损耗78%**。
-- **1883年**：德普勒从法国南部进行**14公里**输电试验，输送功率1.1千瓦，损耗55%。
-- **三线制系统**：1882年英国科学家发明直流三线制系统，外线与中线间电压110伏、两外线间220伏，后扩展到5根线形成直流无限制系统。
-- **技术瓶颈**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难，限制远距离大容量输电。
-- **串联升压试验**：19世纪末法国方剑串联多台直流发电机，将**75千瓦**电力输送**75千米**。
-- **短路器技术**：20世纪初瑞典科学家在串联直流发电机上装短路器，使任意发电机投切不停电；此后20多年建成**15条**直流输电线路。
-- **规模最大线路**：1906年投运的法国慕尼黑水电厂至里昂线路，**180公里、57千伏、4700千瓦**；1927年改建为**260公里、125千伏、19000千瓦**，接入两座水电站。
-- **直流输电局限**：设备复杂、运行方式复杂、造价高、可靠性差。
-## 交流输电发展与交直流之争
-- **变压器前身**：英国法拉第电磁感应原理；美国亨利用多匝线圈做原边、少匝线圈做副边，使高电压感应出低电压。
-- **单相变压器**：1876年俄国科学家发明，主要用于照明。
-- **感应电机**：1883年美国特斯拉制造，具有标志性意义。
-- **并联运行**：1885年匈牙利科学家设计多台变压器并联运行方式，使并联运行成为可能。
-- **爱迪生与凯尔文主张直流**：理由一是直流电效率比交流电高得多；理由二是认为交流电有危险性——曾购买威斯汀豪斯公司的交流发电机卖给监狱给死刑犯执行死刑，以此证明交流电危险。
-- **威斯汀豪斯与特斯拉主张交流**：交流电易利用变压器升压降压，可在电压提高状态下减少电能损失；交流发电机制造业发展为交流输电做了准备。
-- **交流输电示范**：1886年威斯汀豪斯在美国麻省进行**1.2千米、30千伏**交流输电示范；同年又在意大利建成17英里高压输电线路。
-- **三相交流电**：1886年俄国科学家发明三相交流电、三相交流输电和三相异步电动机。
-- **交直流之争标志性工程**：法国到德国的交流输电线路，从水电厂安装三相发电机和升压变压器升压后送到德国，在法兰克福建两座降压变电站——一座供展览会照明，另一座供**100马力**三相异步电动机（用于人工瀑布离心泵）。
-## 输电电压等级提升历程
-- **绝缘子技术**：1898年发明针式绝缘子，美国加利福尼亚输电电压升至**33千伏**；1906年发明悬式绝缘子，建成**110千伏**高压输电。
-- **导线技术**：1912年发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成**154千伏**线路。
-- **均压阀技术**：1923年应用，建成**220千伏**输电线路。
-- **国际里程碑**：1936年美国**287千伏**投运；1952年瑞典**380千伏**投运（**首次采用分裂导线**）；1956年苏联**400千伏**双回线路投运；1965年加拿大**735千伏**投运；1969年美国**765千伏**并入电网；1985年苏联**1150千伏**特高压投运（后降压至500千伏运行）。
-- **国内里程碑**：**220千伏**于1941年投运，**330千伏**于1972年投运，**500千伏**于1981年投运，**1000千伏**于2009年投运（交流特高压标志性首次投运）。
-## 直流输电复兴与国内工程
-- **复兴背景**：交流大电网规模扩大后稳定问题突出，直流在联网中的优势逐渐显露，重新用于电网与电网之间的连接。
-- **首个工业海底电缆工程**：1954年瑞典本土与哥特兰岛之间建成，**100千伏、96公里**，采用汞弧阀技术。
-- **晶闸管换流阀**：1970年瑞典本土与哥特兰岛扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界首个晶闸管换流阀背靠背直流工程在加拿大投运。
-- **中国首个直流工程**：连接舟山群岛与浙江定海电网。
-- **葛上直流**：1989年投运，葛洲坝电厂至上海，**±500千伏**。
-- **云广直流**：今年6月投运的标志性工程，**±800千伏**特高压直流。
-- **课后阅读**：推荐三本书供学生课后阅读，了解电力发展史。
+- **早期直流试验**：电力发展从直流开始而非交流；福泰勒用2000米导线连接瓦斯发电机，拖动直流发电机、电动机和带水泵的电动机，证明直流远距离（两公里）输电可行。
+- **1874年**：俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率**4.5千瓦**，后用于有轨电车的原始工业试验。
+- **1882年**：法国德普勒架设首条**57公里**直流试验线路，采用电报线传输，首端电压343伏、末端850伏，输送功率**200瓦**，损耗**78%**，将水电站直流发电机电力送至博览会。
+- **1883年**：德普勒从法国南部进行**14公里**输电试验，输送功率**1.1千瓦**，从瓦利尔书店到巴黎56公里，损耗**55%**。
+- **1882年10月**：英国科学家发明直流**三线制系统**，外线与中线间电压110伏，两外线间220伏；后扩展到5根线形成直流无限制系统。
+- **直流输电限制**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难，限制远距离大容量输电。
+- **19世纪末**：法国科学家方剑在送端将多台直流发电机**串联**以提高电压，将**75千瓦**电力输送**75千米**。
+- **20世纪初期**：瑞典科学家在串联直流发电机上装**短路器**，使任意发电机投切不停电；此后20多年间建成**15条**直流输电线路。
+- **1906年**：投运法国慕尼黑水电厂到里昂的**180公里、57千伏、4700千瓦**直流线路。
+- **1927年**：改建为**260公里、125千伏、19000千瓦**，接入两座水电站。
+- **直流输电制约因素**：设备复杂、运行方式复杂、造价高、可靠性差。
+- **1954年**：瑞典本土与哥特兰岛间建成**世界第一个工业用海底电缆**直流工程，电压**100千伏**、**96公里**，采用汞弧阀换流。
+- **1970年**：瑞典本土与哥特兰岛间扩建**50千伏、1万千瓦**晶闸管换流阀试验工程。
+- **1972年**：世界上第一个**晶闸管换流阀背靠背直流工程**在加拿大投运。
+- **中国直流工程**：第一个直流输电工程连接**舟山群岛与浙江定海**电网；第二个是1989年**葛上直流**（葛洲坝电厂到上海），±500千伏。
+- **云广直流**：今年6月投运的**±800千伏特高压直流工程**，为标志性工程。
+## 交流输电发展简史
+- **变压器前身**：英国法拉第的电磁感应原理；美国亨利用多匝线圈作原边、少匝线圈作副边，使高电压感应出低电压。
+- **1876年**：俄国科学家发明**单相变压器**，主要用于照明。
+- **变压器串联问题**：法国和英国科学家联合将多台变压器串联到输电线路中，当电弧灯负荷变化时输电电压受干扰。
+- **1883年**：美国特斯拉制造出**感应电机**，为标志性成果。
+- **1885年**：匈牙利科学家设计多台变压器**并联运行**连接方式，使并联运行成为可能。
+- **交直流之争**：爱迪生与凯尔文主张直流电，理由为直流电效率高、交流电有危险性；爱迪生购买威斯汀豪斯公司的交流发电机卖给监狱给死刑犯执行死刑以证明交流电危险。
+- **交流电主张**：威斯汀豪斯和特斯拉主张交流电，因交流电易用变压器升压降压，可在高电压下减少电能损失；交流发电机制造业发展为交流输电做了准备。
+- **1886年**：威斯汀豪斯在美国麻省进行**1.2千米、30千伏**交流输电示范；同年又在意大利建成**17英里、2千伏**高压输电线路。
+- **1886年**：俄国科学家发明**三相交流电、三相交流输电和三相异步电动机**。
+- **交直流之争标志**：从法国到德国的交流输电线路（常被认为是第一条交流输电线路），水电站安装三相发电机和升压变压器，升压后送到德国，在法兰克福建两座降压变电站——一座供展览会照明，另一座供**100马力三相异步电动机**（用于人工瀑布离心泵）。
+- **绝缘技术进展**：1898年发明针式绝缘子，美国加利福尼亚输电电压升至**33千伏**；1906年发明悬式绝缘子，建成**110千伏**高压输电。
+- **1912年**：发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成**154千伏**线路。
+- **1923年**：均压环技术应用，建成**220千伏**输电线路。
+- **1936年**：美国**287千伏**线路投运。
+- **1952年**：瑞典建成**380千伏**线路，**第一次采用分裂导线**。
+- **1956年**：苏联**400千伏**双回线路（平行双回线）投入运行。
+- **1965年**：加拿大建成**735千伏**输电系统。
+- **1969年**：美国**765千伏**线路并入电网。
+- **1985年**：苏联**1150千伏**特高压线路投运，后降压至500千伏运行。
+- **中国电压等级发展**：220千伏于**1941年**投运，330千伏于**1972年**投运，500千伏于**1981年**投运，**1000千伏交流特高压于2009年投运**（国家标志性首次投运成果）。
+- **直流重新受关注**：交流大电网稳定问题突出后，直流在联网中的优势显现，用于电网与电网之间的连接。
 ## 三相交流输电优势
-- **优点一**：易于产生旋转磁场，三相电动机容易做驱动。
-- **优点二**：瞬时功率恒定，不随时间变化。
-- **优点三**：输电线路导线量（金属消耗量）最少。
-- **应用范围**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内大多数高压、超高压、特高压输电采用三相交流，**联网时才采用直流**。
-- **效率比较**：三相三线制传输效率最高；金属消耗量在同等功率和功率因数下最小（全截面为一根导线截面×3）。
-- **结论**：三相三线制因效率最高和金属消耗量最小而在交流输电领域广泛应用，目前仍采用该输电方式。
+- **三相系统优点一**：易于产生旋转磁场，三相电动机容易做驱动。
+- **三相系统优点二**：瞬时功率恒定，不随时间变化。
+- **三相系统优点三**：输电线路导线量（金属消耗量）最少。
+- **应用范围**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内电力系统大多数高压、超高压、特高压输电采用三相交流，**联网时才采用直流**。
+- **三相三线制效率**：在直流传输方式和其他交流传输方式中，**三相三线制传输效率最高**。
+- **金属消耗量比较**：三相三线制全截面为一根导线截面乘以3，在同等功率和功率因数下**金属消耗量最小**。
+- **结论**：因效率最高和金属消耗量最小两个原因，三相三线制在交流输电领域得到广泛应用，至今仍采用。
 ## 电力系统的形成
-- **早期供电方式**：一台发电机向附近负荷供电（如展览会照明、大楼照明），各发电机孤立运行；缺点是一台发电机出问题负荷即停电，**供电可靠性差**。
-- **提高可靠性**：将多台发电机并联连接，一台出问题时另一台可带重要负荷。
-- **输电线路限制**：导线有电阻和电抗两个重要参数，传输功率时产生**电压损耗和功率损耗**；阻抗越大、电流越大，损耗越大，因此输电线路不能太长。
-- **升压原理**：传输有功功率一定时，电压升高则电流减小，有功功率损耗`I²R`和电压降落`IZ`均减小，输电距离可变长。
-- **升压手段**：交流升压采用变压器——送端升压、受端降压，中间电压升上去后距离损耗降低，形成电力系统雏形。
-- **系统化好处**：多台发电机共同供电，一台停机影响不大；可装大机组向大范围供电，机组越做越大，供电范围扩大，**直接带来经济效益**。
-- **中间变电站**：远距离输电（如湖北送华东、云贵送两广）时，在输电线路中间装设变电站降压向当地供电，并可引接部分负荷；输电距离长后出现稳定问题，也可在变电站装设备调整。
+- **单机供电缺点**：一台发电机向附近负荷供电，发电机出问题负荷即停电，**供电可靠性差**（如街边小柴油发电机向商铺供电）。
+- **提高可靠性方法**：将两台发电机并联，一台出问题时另一台可带重要负荷，连接越来越多形成网络。
+- **输电线路参数问题**：导线有**电阻和电抗**两个重要参数，传输功率时产生**电压损耗和功率损耗**；阻抗越大、电流越大，损耗越大，因此输电线路不能太长。
+- **提高电压原理**：传输有功功率一定时，电压升高则电流减小，线路有功损耗（I²R）和电压降落（IZ）均减小，输电距离可变长。
+- **交流升压手段**：采用**变压器**，送端升压、受端降压，中间电压升高后距离损耗降低。
+- **电力系统雏形**：近距离（几十到几百米）发电机可直接相连，远距离则升压传输，多台发电机共同供电形成电力系统雏形。
+- **系统化好处一**：一台发电机停运影响不大，只需发电机数目多于负荷即可保证供电。
+- **系统化好处二**：可装大机组向大片区域供电，完成从**小发电机组向大发电机组**的转变，直接带来经济效益。
+- **远距离输电问题**：距离很长时（如湖北送电华东、云贵送电两广），中间负荷可在输电线路中间装设**变电站**降压供电；稳定问题也可在变电站装设备调整。
 ## 电力系统、电力网与动力系统定义
-- **电力系统定义**：由发电机、变压器、输电线路和用电设备构成的整体，完成电能**生产、输送、分配、消耗**四个环节的职能。
-- **电力网定义**：电力系统中去除发电机和用电设备后的部分，即变压器和输电线路构成的网络。
-- **动力系统定义**：电力系统加上发电厂动力部分——火电厂的锅炉、汽机及煤炭输送处理系统，水电厂的水轮机、水坝、水库等。
-- **概念辨析**：行业中最常用电力网和电力系统两个概念，动力系统概念较少使用；*电力系统比电力网多了发电机（发电厂）和用电设备*。
+- **电力系统定义**：由**发电机、变压器、输电线路和用电设备**构成的整体，完成电能**生产、输送、分配、消耗**四个方面的职能，由发电、输电、配电、用电四个环节组成。
+- **电力网定义**：由**变压器和输电线路**构成的网络，即电力系统中去除发电机和用电设备后的部分。
+- **动力系统定义**：在电力系统基础上加上发电厂动力部分，如火电厂的**锅炉、汽机及煤炭输送处理系统**，水电厂的**水轮机、水坝、水库**等。
+- **概念辨析**：行业中最常说的是**电力网**和**电力系统**两个概念，动力系统概念现在很少说；*电力系统比电力网多了发电机和用电设备，动力系统比电力系统多了动力部分*。
 ## 电网分类
-- **地方电力网**：向固定地方供给电能，电压等级一般在**110千伏及以下**（早期定义35千伏及以下），供电半径**20~50公里**；实例：武汉电网（主要供电电压110千伏和35千伏，少数地方已出现220千伏）。
-- **区域电力网**：电压等级**110、220千伏**及少量**500千伏**，供电半径**超过50公里**，联系较多发电厂和负荷中心；实例：华中电网。
-- **超高压远距离输送网络**：电压等级**500千伏或1000千伏**（东北有330千伏），任务是把发电厂电能送至负荷中心，距离很远，构成跨省跨地区大型电力系统；实例：葛上直流、三峡到上海输电线路、山西晋东南到湖北荆门的特高压系统（跨三省，连接华北和华中电网）。
-- **动态变化**：随着电网发展和电压等级提高，各级电网所用电压等级会发生变化，一般趋势是提高。
+- **地方电力网**：向固定地方供给电能的网络，电压等级一般在**110千伏及以下**（早期定义35千伏及以下），供电半径**20~50公里**。
+- **区域电力网**：电压等级**110、220千伏**及少量500千伏，供电半径**超过50公里**，联系较多发电厂和负荷中心的网络。
+- **超高压远距离输送网络**：电压等级**500千伏或1000千伏**（东北有330千伏），任务是把发电厂电能送到负荷中心，距离很远，构成**跨省跨地区大型电力系统**。
+- **实例一**：武汉电网属**地方电力网**，主要供电电压110千伏和35千伏，少数地方出现220千伏，供电半径一般在50公里以内。
+- **实例二**：华中电网属典型**区域电网**，华中几省紧密联系，供电半径较大。
+- **实例三**：葛上直流、三峡到上海输电线路属**超高压远距离输电网络**，连接华中与华东。
+- **实例四**：山西晋东南到湖北荆门的特高压系统，跨三个省，连接华北电网和华中电网，属超高压远距离输送网络。
+- **电压等级变化规律**：随着电网发展和电压等级提高，各级电网所用电压等级会发生变化，**一般趋向提高**；变电站地位也随之变化。
 ## 变电站分类
-- **按最高电压等级分类**：以站内最高电压命名——华工变电站**10千伏**（10千伏变380伏），关山变电站**220千伏**，凤凰山变电站**500千伏**。
-- **按主要功率流向分类**：大部分功率从高压侧流向低压侧为**降压变电站**；发电厂内大部分功率从低压侧升压至高压侧为**升压变电站**。
+- **按最高电压等级分类**：以站内最高电压等级命名，如华工变电站为**10千伏变电站**（10千伏变380伏），关山变电站为**220千伏变电站**，凤凰山变电站为**500千伏变电站**。
+- **按主要功率流向分类**：以**最主要的功率**流向为准——大部分功率从高压侧流向低压侧为**降压变电站**；发电厂内大部分功率从低压侧升到高压侧为**升压变电站**。
 # 课堂互动与答疑
 **学生**：为什么我国电力系统主要采用交流三相三线制，而不是直流输电？
-**教师**：三相三线制在传输效率上最高，同等功率和功率因数下金属消耗量最小；三相交流易于产生旋转磁场便于电动机制造，瞬时功率恒定不随时间变化。除室内配电等小功率场合用单相交流外，其余基本采用三相交流；国内高压、超高压、特高压输电均用三相交流，仅在联网时采用直流。
-**学生**：电力系统、电力网和动力系统这三个概念有什么区别？
-**教师**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配和消耗；电力网是电力系统去除发电机和用电设备后的部分，即变压器和输电线路构成的网络；动力系统是电力系统再加上发电厂动力部分（如火电锅炉汽机、水电水轮机水坝）。行业中最常用电力网和电力系统两个概念。
-**学生**：地方电力网、区域电力网和超高压远距离输送网络如何区分？
-**教师**：地方电力网电压一般在110千伏及以下（早期35千伏及以下），供电半径20~50公里，如武汉电网；区域电力网电压110、220千伏及少量500千伏，供电半径超50公里，联系较多发电厂和负荷中心，如华中电网；超高压远距离输送网络电压500千伏或1000千伏（东北有330千伏），任务是将电能送至负荷中心，构成跨省跨地区大型电力系统，如葛上直流、三峡至上海线路。
-**学生**：为什么输电距离不能太长？提高电压为什么能解决这个问题？
-**教师**：输电线路有电阻和电抗，电流流过时产生电压损耗和功率损耗，阻抗越大、电流越大损耗越大，距离一长电压降得太低、效率变低。提高电压后传输相同功率时电流减小，有功功率损耗I²R和电压降落IZ均降低，输电距离可变长；交流升压采用变压器，送端升压、受端降压。
+**教师**：三相三线制在传输效率上最高，同等功率和功率因数下金属消耗量最小；三相交流还易于产生旋转磁场、瞬时功率恒定。国内高压、超高压、特高压输电基本采用三相交流，仅在电网联网时才采用直流方式。
+**学生**：电力系统、电力网和动力系统三个概念有什么区别？
+**教师**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配、消耗四个环节；电力网仅含变压器和输电线路，不含发电机和用电设备；动力系统在电力系统基础上再加发电厂动力部分（锅炉、汽机、水轮机等）。行业中最常用的是电力网和电力系统两个概念。
+**学生**：地方电网、区域电网和超高压远距离输送网络如何区分？
+**教师**：按电压等级和供电半径区分：地方电网电压110千伏及以下（早期35千伏及以下），供电半径20~50公里；区域电网电压110、220千伏及少量500千伏，供电半径超50公里；超高压远距离输送网络电压500千伏或1000千伏（东北有330千伏），构成跨省跨地区大型电力系统。武汉电网属地方电网，华中电网属区域电网，三峡到上海线路属超高压远距离输送网络。
+**学生**：为什么输电距离不能太长，提高电压后就能送得更远？
+**教师**：输电线路有电阻和电抗，传输功率时产生电压损耗和功率损耗，距离越长损耗越大、电压降得越低。提高电压后，传输相同功率时电流减小，线路上的有功损耗（I²R）和电压降落（IZ）随之降低，输电距离就能变长。交流升压采用变压器，送端升压、受端降压。
 # 课后任务与学习建议
 ## 复习重点
-- **电力系统四环节**：发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，需建立电力系统整体概念。
-- **电力系统定义**：由发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配和消耗四个环节的职能。
-- **电力网定义**：电力系统中去除发电机和用电设备后的部分，即变压器和输电线路构成的网络；行业中最常用电力网和电力系统两个概念。
-- **动力系统定义**：电力系统加上发电厂动力部分（如火电锅炉汽机、水电水轮机水坝等）；该概念在行业中较少使用。
-- **电力系统特点**：电能不能大量储存，决定了电力系统有功功率和无功功率的动态平衡问题，是进行运行调整和设计的基础原理。
-- **电能质量指标**：需掌握国家标准对电能质量指标的各种规定范围。
-- **额定电压规定**：规定繁杂，需注意寻找额定电压规定之间的基本规律，注意使用条件变化时结论可能失效。
-- **中心点接地方式**：各种中心点接地方式（工作接地）的特点不同，直接影响后续多个章节内容，是比较困难的学习难点。
-- **三相交流优势**：易于产生旋转磁场使三相电动机易做驱动；瞬时功率恒定不随时间变化；输电线路导线量（金属消耗量）最少。
-- **三相三线制**：传输效率最高，金属消耗量在同等功率和功率因数下最小；除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流。
-- **电网分类**：地方电力网（110千伏及以下，供电半径20~50公里）、区域电力网（110、220千伏及少量500千伏，供电半径超50公里）、超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，构成跨省跨地区大型电力系统）。
-- **变电站分类**：按最高电压等级分类（如华工变电站10千伏、关山变电站220千伏、凤凰山变电站500千伏）；按主要功率流向分为升压变电站和降压变电站。
+- **电力系统四个环节**：掌握发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念。
+- **电力系统、电力网、动力系统定义**：电力系统＝发电机＋变压器＋输电线路＋用电设备，完成电能生产、输送、分配、消耗；电力网＝变压器＋输电线路（不含发电机和用电设备）；动力系统＝电力系统＋发电厂动力部分（锅炉、汽机、水轮机等）。
+- **电力系统特点及要求**：电能不能大量储存，决定有功功率和无功功率的动态平衡问题，是运行调整和设计的基础；理解由特点引起的设计、运行、维护方面的基础理论。
+- **电能质量指标**：掌握国家标准对电能质量指标规定的各种范围。
+- **额定电压规定**：规定繁杂，注意寻找额定电压规定之间的基本规律，注意随电网发展各级电网电压等级会提高。
+- **中心点接地方式**：了解电力系统常用接地方式，特别是工作接地（中心点接地方式）的不同特点；该内容直接影响后续多个章节，学习较困难。
+- **电网分类**：地方电力网（110千伏及以下，早期35千伏及以下，供电半径20~50公里）、区域电力网（110、220千伏及少量500千伏，供电半径超50公里）、超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，跨省跨地区）。
+- **变电站分类**：按最高电压等级分类（如10千伏、220千伏、500千伏变电站）；按主要功率流向分为降压变电站（高压侧流向低压侧）和升压变电站（低压侧流向高压侧）。
+- **三相交流输电优势**：易于产生旋转磁场、瞬时功率恒定、输电线路金属消耗量最少；三相三线制传输效率最高，金属消耗量在同等功率和功率因数下最小。
 ## 学习建议
-- **补充前修知识**：对电路理论和电机学知识有欠缺的同学，应补充学习相关内容，特别是变压器和同步电机的知识，本课程对此要求较高。
-- **概念学习方法**：对基本概念注意其内涵和外延，并适当结合实际；从电力系统的特点和要求出发，从最基础的原理进行推导，不要死记结论。
-- **额定电压学习**：注意寻找额定电压规定之间的基本规律，便于记忆繁杂的规定。
-- **接地方式学习**：注意比较各种不同中心点接地方式之间的特点，学完章节后再仔细体会。
-- **课后阅读**：作为电气专业学生应了解电力发展基本史，主讲人推荐三本书供课后阅读，了解交直流输电发展历程。
-- **后续课程衔接**：本课程学后最重要的后续课程为电力系统分析、电力系统机电保护、电力系统自动化和高电压技术四门课。</t>
+- **补充前修知识**：对电路理论和电机学有欠缺的同学，应下去补充相关内容，特别是变压器和同步电机的相关知识，本课程要求较高。
+- **掌握基本概念方法**：注意概念的内涵和外延，并适当结合实际；从电力系统的特点和要求出发，从最基础原理推导，不要死记结论——使用条件变化时结论可能失效。
+- **梳理额定电压规律**：注意寻找额定电压规定之间的基本规律，避免因规定繁杂而混淆。
+- **比较接地方式特点**：注意比较各种不同中心点接地方式之间的特点，为后续章节学习打基础。
+- **课后阅读电力发展史**：作为电气专业学生应了解电力发展的基本历史，推荐三本书供课后阅读，了解交直流输电发展历程及国内外电压等级提升过程。</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>93.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11163/6618</t>
+          <t>11163/7315</t>
         </is>
       </c>
     </row>
@@ -4843,58 +4842,45 @@
       <c r="C14" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本栏围绕调和级数发散性的证明展开，核心议题是评析Stack Exchange上网友给出的多种证明方法。皮卡首先从高中数学出发，定义了级数收敛与发散的基本判据，随后逐一评析了分组估计、柯西凝聚判别法、积分估计、差分法及Stolz定理等证明路径。整体逻辑框架为：以调和级数发散性为锚点，比较不同证明方法的思路与自然程度，并指出部分技巧性证明存在“先射箭后画靶”的刻意构造痕迹。关键概念与结论的细节留给后续各栏展开。
+皮卡在视频中评论了Stack Exchange上关于调和级数发散性的证明，首先介绍了级数收敛与发散的定义，然后逐一评述了网友的证明方法。第一个证明通过分组估计，每组和大于1/2，从而证明发散；皮卡补充了柯西凝聚判别法，指出其证明思路与分组估计完全一致，可推广到非负不增序列。第二个证明使用不等式e^{1/k}&gt;1+1/k，通过连乘积得到H_n&gt;log(n+1)，皮卡认为该证明技巧性强但故弄玄虚，本质与积分估计法相同。积分估计法用积分近似H_n，证明H_n&gt;log(n+1)；差分法使用Stolz定理，通过差分极限为1证明H_n/log n→1，但皮卡认为差分法不自然，因为需要预先知道结果。皮卡总结认为调和级数发散，但不同证明方法有优劣，某些证明故弄玄虚，妨碍理解。
 # 核心概念
-## 调和级数与收敛发散定义
-- **级数收敛**：对正向级数，若存在固定实数 `a` 作为上界，使得所有前 `n` 项和 `sn` 均小于 `a`（无论 `n` 取多大），则称该级数**收敛**。
-- **级数发散**：若存在一个单调递增且无上界的序列 `bn`，使得 `sn` 大于 `bn`，即对任意大的数 `b`，总能通过增大 `n` 使 `bn` 超过 `b`，则称该级数**发散**。
-- **调和级数**：形如 `1 + 1/2 + 1/3 + … + 1/n` 的级数，其部分和记为 `hn`（或 `sn`），英文为 `harmonic`，是调和序列的部分和。
-- **调和级数发散**：`hn` 无上界，因此调和级数发散；这是高等数学中的经典结论。
-## 分组求和与柯西凝聚判别法
-- **分组估计法**：将调和级数各项分组，如 `{1}`、`{1/2, 1/3}`、`{1/4, 1/5, 1/6, 1/7}`、`{1/8, …, 1/15}` 等，每组和均大于 `1/2`，因组数无限，故级数发散。
-- **柯西凝聚判别法**：其证明思路与分组估计法完全一致——对非负不增序列分组并做上下界估计，从而将原级数的收敛发散性转化为凝聚后序列的收敛发散性。
-- **凝聚判别法应用**：对 `∑1/n` 应用该判别法，等价于判断 `∑(2^k × 1/2^k) = ∑1` 的收敛性，而无穷个 `1` 相加显然无上界，故发散。
-- **分组求和思想**：高斯幼年计算 `1+2+3+…+100` 时，采用 `1+100=101`、`2+99=101` 的分组配对法，只需数出有多少个 `101` 即可；在求和或估计问题中，若能发现具有良好性质（如和恒定、满足估计要求）的组，问题即可简化。
+## 级数收敛与发散
+- **收敛**：对于正向级数，若存在固定实数a，使得所有部分和s_n都小于a，则级数收敛。
+- **发散**：若部分和s_n大于某个无界递增的b_n，即对任意大的数b，总能通过增大n使b_n超过b，则级数发散。
+## 分组估计法
+- 第一个网友的证明：将调和级数分组，每组和大于1/2，如1/2+1/3&gt;1/2，1/4+1/5+1/6+1/7&gt;1/2，以此类推，从而证明发散。
+- 皮卡指出，这种分组求和思路与高斯求和（1+2+…+100）类似，核心是发现具有良好性质的组，将求和问题转化为计数问题。
+## 柯西凝聚判别法
+- 证明过程与分组估计完全一致，通过分组取上界或下界，将原级数的收敛性转化为加速序列的收敛性。
+- 适用于非负不增序列，如调和级数∑1/n的收敛性等价于∑2^k·(1/2^k)=∑1，后者显然发散。
 ## 积分估计法
-- **积分近似思想**：`hn` 从几何上可视为一系列高为 `1/n`、底为 `1` 的矩形面积之和，这些矩形始终大于对应曲边梯形（即 `1/x` 曲线下的面积），故 `hn` 大于积分 `∫₁ⁿ⁺¹ 1/x dx = log(n+1)`。
-- **发散结论**：`log(n+1)` 无上界，因此 `hn` 也无上界，级数发散；该方法属于**和的积分估计**流派。
-## 差分法与指数放缩
-- **指数放缩法**：利用 `e^(1/k) &gt; 1 + 1/k`（即 `e^x &gt; 1+x`），对 `e^(hn)` 做放缩，将和转化为连乘积。
-- **连乘积化简**：`∏(1 + 1/k) = ∏((k+1)/k)`，相邻项相消后等于 `n+1`，从而证明 `hn &gt; log(n+1)`。
-- **对数差分关系**：该方法与对数不等式 `log(k+1) - log(k) &lt; 1/k` 的差分求和本质相同——两边取对数后即为上述指数放缩法，两种表述完全等价。
-## Stolz定理证明的批评
-- **Stolz定理**（中文亦称 `stolz` 定理）：当分子分母均为无穷大时，可通过比较差分 `(aₙ₊₁ - aₙ)/(bₙ₊₁ - bₙ)` 的极限来求 `aₙ/bₙ` 的极限。
-- **应用方式**：证明 `hn/log n` 的极限为 `1`，其差分分别为 `1/(n+1)` 和 `log(1 + 1/n)`，两者比值极限为 `1`，故 `hn` 与 `log n` 同增长级别，`log n` 无上界，所以 `hn` 发散。
-- **不自然之处**：该方法需预先知道 `hn` 与 `log n` 同阶这一结论才能构造差分，属于**先射箭后画靶**；若不知道结果，没有理由选择 `log n` 而非 `log log n` 的平方或 `√n` 作为比较对象。
-- **调和级数基本估计**：`log(n+1) &lt; hn &lt; log n + 1`，两边除以 `log n` 后取极限即得 `hn/log n → 1`；但证明该不等式仍需回到积分估计等方法，并非独立的新方法。
+- 用积分曲线面积近似H_n，因H_n的几何意义是矩形面积，始终大于下方曲边梯形面积，故H_n&gt;∫1/x dx=log x，从而得到H_n&gt;log(n+1)。
+- 皮卡认为这是正规流派，但笔记中内容较多，未详细展开。
+## 差分法（Stolz定理）
+- 通过比较H_n与log n的差分，分子差分（H_{n+1}-H_n=1/(n+1)）和分母差分（log(n+1)-log n=log(1+1/n)）的极限为1，从而证明H_n/log n→1。
+- 皮卡认为此法不自然，因为需要预先知道结果才能选择log n作为比较对象。
 # 核心结论
 ## 核心结论
-- **调和级数发散**：级数 ∑1/n（即 1+1/2+1/3+…+1/n+…）是发散的，不存在一个固定实数上界能控制其所有部分和。
-- **收敛与发散的定义**：对正项级数，若所有部分和 sn 都小于某个固定实数 a（无论 n 取多大），则收敛；若部分和大于某个单调递增且无上界的 bn，则发散。
-- **第一个网友的证明**：将调和级数分组（1 单独一组、1/2+1/3 一组、1/4+1/5+1/6+1/7 一组、1/8～1/15 一组……），每组和都大于 1/2，而组数无限，故部分和无上界，级数发散。
-- **柯西凝聚判别法**：对非负不增序列，其级数收敛发散性质等价于加速后的序列 ∑2^k·a(2^k)；用于调和级数时，等价于 ∑2^k·(1/2^k)=∑1，即无穷个 1 相加，显然发散。
-- **第二个网友的证明**：证明 hn &gt; log(n+1)，因 log(n+1) 无上界，故 hn 也无上界，级数发散。
-- **积分估计法**：用积分曲线面积近似 hn，矩形面积始终大于下方曲边梯形面积，可推出 hn &gt; log(n+1) 的下界。
-- **差分法**：利用 e^(1/k) &gt; 1+1/k，将 e^hn 放缩为连乘积 ∏(1+1/k)，相邻项相消后等于 n+1，从而证明 hn 发散。
-- **Stolz 定理证明**：通过 hn/log n 的差分（分子差分为 1/(n+1)，分母差分为 log(1+1/n)）求极限为 1，从而证明 hn 与 log n 同增长级别，log n 无上界故 hn 发散。
+- 调和级数∑1/n是发散的，因为其部分和H_n无上界。
+- 柯西凝聚判别法可推广到非负不增序列，其证明思路与分组估计完全一致。
+- 积分估计法证明H_n&gt;log(n+1)，因log函数无上界，故H_n发散。
+- 差分法通过Stolz定理证明H_n/log n→1，从而说明H_n与log n同增长级别，但皮卡认为此法不自然。
 ## 易混点与适用边界
-- **收敛与发散判断的适用前提**：上述简化判断仅适用于正项级数（原文明确「因为是正向技术，所以我们只需要考虑两个判断」）。
-- **柯西凝聚判别法的适用条件**：仅适用于非负不增序列；其证明思路与分组求和完全一致，本质是分组后对每组做上下界估计。
-- **积分估计法的几何边界**：矩形面积始终大于曲边梯形面积，故 hn 大于积分值；该放缩方向是单向的（只给出下界）。
-- **差分法对微积分的依赖**：e^(1/k) &gt; 1+1/k 本身需用微积分证明，而微积分建立在极限之上；原文指出也可用不等式 (1+1/k)^k &lt; e 在不用微积分的情况下操作，但用微积分更简单。
-- **Stolz 定理的适用前提**：适用于分子分母均为无穷大的情形，通过比较差分极限来求原极限；但原文强调该证明「不自然」，因为需要预先知道 hn 与 log n 同阶这一结果才能构造差分，属于「先射箭后画靶」。
-- **log 记号的地区差异**：原文指出 log 是美国写法，ln 是欧洲写法（经苏联传入中国），两者指同一函数。
-- **常见误区**：皮卡批评某些证明「故弄玄虚」——用障眼法包装简单本质，妨碍理解但让人感觉 magic；差分法看似巧妙，实际与对数差分不等式两边求和是同一回事。
+- 收敛与发散的定义：收敛要求所有部分和小于某个固定上界，发散则要求部分和无界递增。
+- 柯西凝聚判别法仅适用于非负不增序列，不适用于一般级数。
+- 差分法需要预先知道结果（如H_n/log n→1）才能选择比较对象，否则难以自然想到。
+- 积分估计法依赖于微积分知识，而e^{1/k}&gt;1+1/k不等式本身需要微积分证明，但也可用中学知识近似。
 ## 待澄清问题
-- **后续内容安排**：皮卡表示后面还有很多证明方法，若本期反响不错则出下一期，再找帖子或网友投稿来评论，具体选题未定。</t>
+- 皮卡提到“dialectic分解”思路，但表示“一时半会也讲不清楚”，留待后续。
+- 皮卡表示“后面还有很多方法，我们有机会再评论”，并计划根据反响决定是否出下一期。</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>33.5</v>
+        <v>54.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7465/3201</t>
+          <t>7465/1465</t>
         </is>
       </c>
     </row>
@@ -4957,72 +4943,74 @@
       <c r="C15" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本期视频由工作室老李（发言者2）主讲，围绕GitHub这一全球开源资源库，介绍实用热门项目与使用技巧。内容分为三块：一是推荐工作性价比评估、表情包合集、健康指南、一键证件照、自重健身指导、教材合集、声音克隆、AI学习资源库等实用项目；二是针对国内访问GitHub困难，介绍Watt Toolkit加速软件、镜像站、魔法（VPN）三种解决方案；三是讲解页面汉化、原生搜索局限与AI辅助搜索方法，并说明项目主页中star、watch、fork、read me文件等核心元素的作用。整体逻辑从「找资源」到「上得去」再到「用得好」，层层递进。
+本次分享会由工作室老李主讲，围绕GitHub这一全球性开源资源平台展开，核心议题包括两大板块：一是介绍平台上实用、热门的开源项目，二是解决国内用户访问GitHub时常遇到的网络不通、页面全英文、原生搜索不好用等问题。整体逻辑框架为“项目展示—问题解决—技巧演示”，先通过多个具体项目（如工作性价比评估、表情包合集、AI工具等）展示平台价值，再针对访问、汉化、搜索三大痛点逐一给出解决方案，并讲解项目页面的基本结构与判断项目活跃度的方法。分享基调为实用导向，所有提及项目与技巧均整理成文档供观众领取。
 # 核心概念
 ## GitHub 实用项目
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事评价等因素，综合输出工作性价比分数和评级；演示中程序员岗位获评「性价比还不错，优质牛马」。
-- **表情包博物馆**：收录国内过去全网爆火的表情包大合集，含甄嬛传、罗翔、特朗普、马保国等主题，可用于斗图。
-- **健康活到150岁指南**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢与炎症自愈、吃天然发酵类食品改善肠道菌群生态。
-- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照及各种规格打印模板。
-- **自重健身教练项目**：选择目标肌肉群（如腹肌）后提供自重训练参考动画，适合请不起真人教练的用户。
-- **教材合集项目**：收集国内小学、初中、高中及部分大学PDF教材，全部免费使用。
+- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等，综合评估后给出工作性价比分数和评级；演示中程序员岗位获评「性价比还不错，优质牛马」。
+- **表情包博物馆**：收录国内过去几年全网爆火的表情包大合集，含甄嬛传、罗翔、特朗普、马保国等主题，可用于斗图。
+- **健康活到150岁指南**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态。
+- **一键做证件照项目**：上传大头照即可一键抠图换背景，生成不同标准的证件照和多种规格打印模板。
+- **丐版健身教练项目**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，无需健身器材或真人教练。
+- **教材合集项目**：收集国内所有小学、初中、高中及部分大学的PDF教材，全部免费使用。
 - **全自动视频生成项目**：即 `morning printer Turbo`，近期热门。
-- **声音克隆模型 `ChatBox TTS`**：零样本语言克隆，情感控制到位，克隆声音接近真人；可上传音频合成英文台词试听效果。
+- **声音克隆模型 `ChatBox TTS`**：零样本语音克隆，情感控制到位，克隆声音接近真人；上传自己的音频即可合成指定台词。
 - **AI学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术，作者整理成500多页PDF文档，含大量示意图。
-- **`awesome AI Apps` 项目**：收录大模型最新agent应用，如医学影像数据分析agent、AI投资agent、竞争对手情报分析agent，可跟进AI落地案例或寻找创业点子。
-## GitHub 访问加速
-- **Watt Toolkit 加速软件**：进入官网选择适合电脑的版本下载安装，打开后找到网络加速勾选GitHub加速即可流畅访问；对大多数人而言是更流畅的选择。
-- **镜像站**：如 `gh-proxy`，浏览器点开直接访问GitHub，默认显示镜像项目地址，也可搜索其他项目；速度与稳定性较Watt Toolkit差。
-- **魔法（VPN）**：发言者2个人最推荐的方法。
-- **GitHub注册**：用国内QQ邮箱即可完成注册。
+- **`awesome AI Apps` 项目**：收录大模型最新的Agent应用，如医学影像数据分析Agent、AI投资Agent、竞争对手情报分析Agent等，可用于跟进AI应用落地案例或寻找创业点子。
+## GitHub 访问技巧
+- **Watt Toolkit 加速软件**：进入官网选择适合电脑的版本下载安装，打开后找到网络加速并勾选「GitHub加速」，即可流畅访问。
+- **GitHub 镜像站**：如 `gh-proxy`，浏览器点开即可直接访问GitHub，默认是镜像的项目地址，也可搜索其他项目；速度和稳定性比加速软件差。
+- **VPN（魔法）**：主讲人个人最推荐的方式，需自行注册GitHub账号，用国内QQ邮箱即可注册。
 ## GitHub 页面汉化
-- **翻译插件**：谷歌浏览器推荐安装谷歌翻译或沉浸式翻译，可将网页直接翻译成中文，翻译效果基本够用；安装路径为「三个点 → 拓展程序 → 管理拓展程序 → 搜索插件名安装」。
-- **汉化插件**：动手能力强的用户可额外安装，同为GitHub项目。
+- **浏览器翻译插件**：谷歌浏览器推荐 `谷歌翻译` 或 `沉浸式翻译`，安装后可将网页直接翻译成中文，翻译效果基本够用；安装路径为「三个点 → 拓展程序 → 管理拓展程序 → 搜索插件名安装」。
+- **汉化插件**：动手能力强的用户可额外安装，实现更彻底的界面汉化。
 ## GitHub 搜索方法
-- **原生搜索**：顶部搜索框按与搜索词匹配度排序，常用按star数排序；但按精准匹配搜索，如搜 `screen record` 与 `screen recording` 结果不同，对中文用户不友好。
-- **AI搜索（推荐）**：在ChatGPT中用中文提出需求（如「在GitHub上帮我找好用的录屏软件」），AI可汇总热门项目并整理成表格，覆盖原生搜索因词形差异漏掉的项目。
-## 项目主页要素
-- **项目本质**：GitHub上的一个项目本质上是一个文件夹，项目名字下是子文件夹或文件。
-- **`watch` / `fork` / `star`**：watch是关注项目，fork是复制项目到自己的账号，star相当于收藏和点赞；star数即项目的江湖地位，越多越受欢迎。
-- **`about`**：项目简介，一句话说明项目用途。
-- **开源协议与`release`**：release处为软件安装包，可下载最新版本安装使用。
-- **`read me` 文件**：项目说明书，默认在项目最下方展开显示，介绍项目用途、安装使用方法，是了解项目必看内容。
-- **`commit` 日期**：即最近更新时间；若更新日期在几年前，大概率是无人维护的僵尸项目。
-- **`explore` → `trending`**：可查看全站当天、本周、本月最热门项目，适合跟踪最新热门开源项目。
-- **AI跟踪热门项目**：让ChatGPT找GitHub daily，可及时获取最新最热门项目分享。
+- **原生搜索**：顶部搜索框输入关键词（如录屏的英文 `screen record`），默认按与搜索词的匹配度排序；更常用的是按 `star` 数排序，star越多代表项目越受欢迎、江湖地位越高。
+- **原生搜索的局限**：按搜索词精准匹配，如搜 `screen record` 与 `screen recording` 按星标排序结果不同，导致英文不好时搜得不够准确、全面。
+- **AI 搜索（推荐）**：在ChatGPT中用中文提问（如「在GitHub上帮我找好用的录屏软件」），AI可搜齐热门工具并总结成表格，弥补精准匹配的不足。
+## GitHub 项目页面结构
+- **项目本质**：GitHub上的一个项目本质上是一个文件夹，项目名字下面是子文件夹或文件。
+- **`watch` / `fork` / `star`**：分别对应关注项目、复制项目到自己的账号、收藏和点赞（一键三连）。
+- **`About` 简介**：项目右侧的一句话简介，说明项目是干什么的。
+- **`Release` 安装包**：存放软件的安装包，点开可看到最新版本并下载安装。
+- **`Readme` 文件**：项目的说明书，默认在项目最下面展开显示，用于了解项目用途、安装使用方法，是了解一个项目必看的内容。
+- **`commit` 日期**：每个文件最近的提交日期即最近更新时间；若更新日期是好几年前，大概率是无人维护的僵尸项目。
+- **`Explore` → `Trending`**：可查看全站当天、本周、本月最热门的项目，适合跟踪最新热门开源项目。
+- **AI 获取热门项目**：让ChatGPT找 `GitHub daily`，可及时分享各种最新最热门的项目。
 # 核心结论
 ## 核心结论
-- **GitHub 是资源宝库**：几乎想找的资源、教程、工具都能找到，包括麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂面试题和面试经验，Google、阿里等公司最新开源大模型，AI 副业赚钱教程等。
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等，综合输出工作性价比分数和评级；发言者2测试程序员工作，评估结果为「性价比还不错，优质牛马」。
-- **表情包博物馆项目**：收录国内过去这些年全网爆火的表情包大合集，包括甄嬛传、罗翔、特朗普、马保国等主题。
-- **健康活到150岁指南**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态等。
-- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照和各类规格打印模板。
-- **自重健身指导项目**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，适合请不起真人教练的用户。
-- **教材合集项目**：收集国内所有小学、初中、高中及一部分大学的 PDF 教材，全部免费。
-- **声音克隆模型 ChatBox TTS**：零样本语言克隆，情感控制到位，克隆声音像真人说话；上传自己的音频可合成英文台词。
-- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
-- **Awesome AI Apps 项目**：收录大模型最新的 Agent 应用，如医学影像数据分析 Agent、AI 投资 Agent、竞争对手情报分析 Agent 等，可用于跟进 AI 应用落地案例或找创业点子。
-- **GitHub 访问三种解决方案**：① Watt Toolkit 加速软件——进入网站选适合电脑的版本下载安装，打开后找到网络加速勾选 GitHub 加速，更流畅稳定；② 镜像站（如 gh-proxy）——浏览器直接访问，可搜索 GitHub 其他项目，但速度和稳定性较差；③ 魔法（VPN）——发言者2个人最推荐的方法。
-- **GitHub 注册**：用国内 QQ 邮箱即可完成注册。
-- **页面汉化方案**：谷歌浏览器推荐安装谷歌翻译或沉浸式翻译插件，可将网页直接翻译成中文；动手能力强的可安装汉化插件。
-- **AI 搜索替代原生搜索**：GitHub 原生搜索按关键词精准匹配，如搜 screen record 和 screen recording 按星标排序结果不同；用 ChatGPT 等 AI 工具用中文提问（如「在 GitHub 上帮我找好用的录屏软件」），可搜齐热门工具并总结成表格，解决英文不好、搜索不准确不全面的问题。
-- **项目主页要素**：star 数代表项目江湖地位和受欢迎程度，watch 是关注，fork 是复制到自己的账号，star 相当于收藏和点赞；about 是项目简介；release 是软件安装包，可下载最新版本；read me 文件是项目说明书，默认在项目最下面展开显示，是了解项目必看的内容。
-- **判断僵尸项目**：查看每个文件最近的 commit 日期（即最近更新时间），若更新日期是好几年前，大概率是没人维护的僵尸项目。
-- **跟踪热门项目**：点开左侧 explore 的 trending，可查看全站当天、本周、本月最热门的项目；也可让 ChatGPT 找 GitHub daily，及时分享最新最热门的项目。
+- **GitHub 定位**：GitHub 不只是代码托管平台，而是几乎能找到资源、教程、工具的巨大宝藏资源库，包含名校公开课（麻省理工、斯坦福）、大厂面试题与面试经验（字节、阿里、腾讯）、大公司最新开源大模型（Google、阿里）、AI 副业教程等正经内容，以及表情包合集、养生指南、大厂黑名单等非正经内容。
+- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事评价等因素，综合给出工作性价比分数和评级；主讲人测试其程序员工作，评估结果为「性价比还不错，优质牛马」。
+- **表情包博物馆项目**：收录国内过去几年全网爆火的表情包大合集，含甄嬛传、罗翔、特朗普、马保国等主题。
+- **健康活到 150 岁指南项目**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态。
+- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照和多种规格打印模板。
+- **健身教练项目**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，适合请不起真人教练的用户。
+- **教材合集项目**：收集国内所有小学、初中、高中及部分大学 PDF 教材，全部免费。
+- **全自动视频生成项目**：即 Morning Printer Turbo，为近期热门项目。
+- **声音克隆模型 ChatBox TTS**：零样本语音克隆，情感控制到位，克隆声音像真人说话；上传自己的音频可合成英文台词。
+- **AI 学习资源库项目**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
+- **Awesome AI Apps 项目**：收录大模型最新 Agent 应用，如医学影像数据分析 Agent、AI 投资 Agent、竞争对手情报分析 Agent，可用于跟进 AI 应用落地案例或寻找创业点子。
+- **GitHub 访问方案**：国内访问 GitHub 又卡又难，提供三种方法——Watt Toolkit 加速软件（进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选 GitHub 加速）、GitHub 镜像站（如 gh-proxy，浏览器点开直接访问，可搜索 GitHub 其他项目）、VPN（魔法，主讲人个人最推荐）。
+- **页面汉化方案**：给浏览器安装翻译插件，谷歌浏览器推荐谷歌翻译或沉浸式翻译，可将网页翻译成中文；动手能力强的可安装汉化插件。
+- **GitHub 搜索方法**：原生搜索按搜索词精准匹配排序，如搜 screen record 和 screen recording 按星标排序结果不同；推荐用 ChatGPT 等 AI 搜索，用中文提问即可汇总热门录屏工具并总结成表格。
+- **项目页面结构**：GitHub 项目本质是文件夹，项目名字下面是子文件夹或文件；Watch 是关注项目，Fork 是复制项目到自己的账号，Star 相当于收藏和点赞；About 是项目简介；Release 是软件安装包，可下载最新版本。
+- **Readme 文件**：是项目说明书，默认在项目最下面展开显示，可了解项目用途、安装使用方法，是了解项目必看的内容。
+- **项目维护判断**：通过每个文件最近的 commit 日期判断，可理解为最近更新时间；更新日期是好几年前的，大概率是没人维护的僵尸项目。
+- **热门项目追踪**：点开左侧 Explore 的 Trending，可查看全站当天、本周、本月最热门项目；也可让 ChatGPT 找 GitHub daily，及时分享最新最热门项目。
 ## 易混点与适用边界
-- **Watt Toolkit 与镜像站对比**：Watt Toolkit 加速软件更流畅、稳定，是更优选择；镜像站（gh-proxy）速度和稳定性更差，仅作备选。
-- **原生搜索与 AI 搜索对比**：原生搜索按搜索词精准匹配，同一含义的不同英文写法（如 screen record 与 screen recording）搜出结果不同，对中文用户不友好；AI 搜索可弥补英文不好、搜索不准确不全面的问题。
-- **watch、fork、star 的区别**：watch 是关注项目，fork 是复制项目到自己的账号，star 相当于收藏和点赞，三者功能不同。
-- **read me 文件的作用**：相当于项目说明书，与公园相亲角贴的内容本质上是一回事，通过它可了解项目用途、安装使用方法。
-- **commit 日期判断项目状态**：commit 日期即最近更新时间，更新日期在好几年前的项目大概率是无人维护的僵尸项目。</t>
+- **三种访问方式对比**：Watt Toolkit 加速软件对大多数人更流畅；镜像站速度和稳定性更差；VPN（魔法）为主讲人个人最推荐，但需自行解决获取方式。
+- **GitHub 原生搜索局限**：按精准匹配排序，同一含义的不同英文表达（如 screen record 与 screen recording）搜索结果不同，对英文不好、搜索内容不准确不全面的用户不友好。
+- **Star 数与项目质量**：Star 数代表项目受欢迎程度（江湖地位），Star 越多项目越受欢迎，但原文未说明 Star 数与项目质量直接等同。
+- **commit 日期判断**：commit 日期可理解为最近更新时间，多年未更新大概率是僵尸项目，但原文未给出具体年限标准。
+- **镜像站使用限制**：默认是镜像的项目地址，但搜索 GitHub 其他项目没有问题。
+- **GitHub 注册**：注册很简单，用国内 QQ 邮箱就可以。</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>39.6</v>
+        <v>39.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4014/3925</t>
+          <t>4014/4076</t>
         </is>
       </c>
     </row>
@@ -5393,67 +5381,68 @@
       <c r="C16" t="inlineStr">
         <is>
           <t># 访谈概述
-本期《锵锵三人行》围绕日本历史剧《大奥》与《明朝那些事儿》展开，探讨中日文化差异及明朝历史特点。受访者为《明朝那些事儿》作者当年明月（发言者2）与嘉宾马先生（发言者3），主持人窦文涛（发言者1）及另一位嘉宾（发言者4）参与对话。访谈主线分两大板块：一是借《大奥》热播解读日本文化中的极端精神、忠诚文化与中日文化差异；二是围绕明史研究难点、明朝兴亡经验教训及明代皇帝趣事展开讨论。受访者核心观点包括：日本文化体现极端精神与忠诚文化，与中国中庸文化形成对比；明史资料最多但一个事件可能有7种不同说法，研究需注意史料矛盾；历史经验教训不能简单套用，引用「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」。关键锚点包括《大奥》《明朝那些事儿》、德川家康、1644年明朝灭亡。访谈看点在于当年明月指出正德皇帝被嘉靖时期编写的实录抹黑、实际有城府，以及明末北京可能闹瘟疫（疙瘩瘟，即天花）导致李自成军入城无人抵抗等与流俗看法不同的观点。
+本期《锵锵三人行》围绕日本历史剧《大奥》与明朝历史展开，主持人窦文涛与嘉宾马未都、《明朝那些事儿》作者当年明月（石悦）等对谈，对比中日文化差异，并延伸至明朝历史特点与历史研究难点。关于《大奥》，嘉宾认为它是《大长今》之后最有影响的外国电视剧，其历史背景对应中国晚明到清初及明治维新前；讨论指出日本文化体现极端精神，所有事情做到尽头，与中国的“中庸”文化形成鲜明对比，日本社会鄙视投机取巧，终身雇佣制下跳槽率最低，民族重视死亡，经济危机时身家万贯者剖腹自杀。关于明朝历史，当年明月表示明史资料最多，但同一事件可能有7个不同说法；朱元璋从乞丐当上皇帝，独此一份，定下明朝规章制度基本无大改动；明末市民生活轻松，江浙工商业兴起，三言二拍等娱乐产品出现；1644年明朝灭亡时北京闹瘟疫（疙瘩瘟，可能为天花）。关于明朝皇帝，讨论涉及明武宗正德要去江南被大臣跪金水桥抗议、打死十几人仍不让去，正德到扬州要东西政府不给、让人把酒席折成银两带回；天启帝爱当木匠，干完活让大臣去卖，卖得好有成就感。嘉宾认为正德皇帝被评价为最荒淫可能因嘉靖非其亲生，编史有偏颇。
 # 访谈详细记录
-## 日本历史剧《大奥》与文化解读
-- **《大奥》热播反响**：发言者3认为《大奥》是继《大长今》以后最有影响的外国电视剧，发言者2表示赞同，认为它确实是一部拍得非常好的剧。
-- **剧情时段**：发言者3介绍《大奥》共三部，前两部相当于中国的晚明到清初时段；发言者2补充第三部在明治维新之前，是一部有跨越性的历史剧。
-- **吸引点**：发言者2称是临时翻到才看，吸引他的是剧中体现的严谨精神——回头看《三国演义》会看到群众演员笑，但日本历史剧看不到笑的，每个人都特别有专业精神。
-- **大奥含义**：发言者3解释大奥即普通话的后宫，日语「奥」指屋子最深处，如「堂奥」「深奥」；发言者2补充另一层意思是一般人不准进去。
-- **日本权力结构**：发言者2指出天皇一直是摆设，实际掌权的是幕府将军；德川家康开创德川幕府后权力集中在一人手上，想干什么就干什么。
-- **天皇处境**：发言者2称天皇一点都不受崇拜，曾研究日本战国历史时发现天皇有一段时间没人待见——天皇想办活动没钱找将军要，将军不给，活动没办成，天皇后来为抗议幕府而退位。
-- **日本极端精神**：发言者2认为从《大奥》可看出日本文化从头到尾没变，即「极端精神」——所有事情要做到尽头；发言者3补充这是每个人发自内心的，与中国不同。
-- **战后经济成就**：发言者3称日本1945年战后用30年成为世界第二经济强国，是绝对量而非人均量，且是世界上唯一没有资源的强国，这不是偶然而是必然。
-- **中日文化对比**：发言者2称中国文化精神是中庸，日本精神恰相反，坚持一个原则做到极致——如炮手开炮时忘记所有事情只记得把这一炮开出去，就达到最高境界。
-- **忠诚文化**：发言者3称日本是忠诚文化的典型国度，如《大奥》第一集阿福25岁进去当奶妈、65岁去世，40年无论做什么事完全出于公心，所有人最终都认为她是楷模。
-- **终身雇佣制**：发言者2称西方经济学家不能理解日本终身雇佣制——缺乏竞争理应导致效率低下，但日本终身雇佣下积极性仍特别高；发言者3补充日本跳槽率最低，每次跳槽都是社会资源浪费。
-- **豆腐厂见闻**：发言者3称参观日本最底层工厂时，豆腐厂规定当天做当天卖，夜里11:45所有人坐好看着表，12点整一齐站起来开始工作，到四点多干完上市，没人闲聊。
-- **岛国生存观**：发言者2认为日本是岛国，没有资源还常火山地震，跑都没地方跑，人对世界有极强求生欲望或悲观感，必须融入团体按固定规则做事才能生存。
-- **投机者无生存环境**：发言者3称日本投机取巧的人没有生存环境，社会文化鄙视非常难过；举例日本做绳子做到全日本第一的人，几年内不赚钱铺市场，之后靠两边各加2%赚到4%的利润。
-- **「慢慢来才是最快」**：发言者2引用别人讲过的话「慢慢来才是最快的方法」，所有人按自己角色做事最节省成本，不会互相抵消，形成合力非常可怕。
-- **是否愿做日本人**：发言者3称在这种文化中愿意也做不成，文化不允许这种现象生存；发言者2表示很不愿意，因为日本人很多时候盲从，且有寻死的潜在欲望。
-- **死亡观**：发言者2认为日本人看樱花只看落的那天，对死亡不是藐视而是有点向往或不惧怕，二战日军在华暴行是藐视生命的行为；发言者3不同意，认为日本民族不是藐视生命而是重视死亡，经济危机时很多身家万贯的人剖腹自杀。
-## 明朝历史与《明朝那些事儿》
-- **写作缘由**：发言者2称写明朝是因为明史资料最多——明实录几千万字，加上明通鉴、明史纪事本末、明会典等堆得比山还高，但一个事件可能有7种不同说法，像黑泽明电影《罗生门》一样。
-- **明朝历史特点**：发言者3指出明朝260多年过程本身跌宕起伏，几次要死没死成，如土木堡之变、夺门之变等，皇上被瓦剌军抓了又扶弟弟上位，完全构成现代版电视剧情节。
-- **推崇朱元璋**：发言者2认为朱元璋从乞丐到最后推翻元朝当上皇帝，定下明朝规章制度且基本没有大改动，是了不起的人才；发言者3补充历史上最底层的人坐到最上面独此一份，刘邦好歹是亭长。
-- **英雄史观**：发言者3认为人的因素最大，改变时势一定出现一个人；发言者2称朱元璋天分相当高，如《亮剑》中李云龙没上过军事院校能打仗，是战场上积累经验的天赋。
-- **朱元璋起义**：发言者2称朱元璋因汤和来信被告发、没办法才去起义，当时是造反要掉脑袋的事，旁观者觉得好玩，实际非常有风险。
-- **历史研究态度**：发言者2强调历史最重要的是弄明白它是发生过的，很多人看历史觉得故事好玩，但不好玩；发言者3补充站在历史原点时前后都看不见，必须撤出来才能看见。
-- **晚明生活**：发言者2称明末很多真相被掩盖，当时市民生活特别轻松舒服，想去哪去哪，江浙一带兴起工商业，给人当雇工活得很滋润，《三言二拍》这类娱乐产品出现说明有养活自己的资本；发言者3补充晚明工艺变得非常精细，文征明、唐寅、董其昌都是那个时期的人。
-- **明末瘟疫**：发言者2称1644年李自成军打到京城无人抵抗，有史料记载当时北京闹瘟疫叫疙瘩瘟（即天花），他曾与老师王佩奇交流说明朝亡得真蹊跷，什么坏事衰事都赶上了。
-- **王朝300年大限**：发言者3称中国历史王朝300年是大限，严格讲跨过300年的只有宋朝（南北宋接上，319年），汉朝中间隔断14年不能比，唐朝、明朝、清朝都没跨过；发言者2比喻一公司成立200多年够本了。
-- **历史教训**：发言者2称「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因为历史事件发生时有背景，史书记载下来的是照片，而古人的生活是录像，不知道那一幕之前和之后是什么，不能套用经验。
-- **明朝皇帝趣事**：发言者2称明朝什么都能发生——宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣），皇帝出去了还能回来做皇帝；吴三桂与满清合作入关是为崇祯皇帝复仇。
-- **正德皇帝**：发言者2认为正德皇帝被写坏了——明武宗实录是嘉靖指派杨廷和等人编的，嘉靖是堂兄弟接班，不能把前朝皇帝写太好；正德从江南回来先在通州停半天派人打探京城有无埋伏，说明他很有城府。
-- **天启皇帝当木匠**：发言者3称天启皇帝干完活差大臣去卖，回来还打听卖得怎么样，卖得很好成就感特大；这从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然。
-- **明式家具与审美**：发言者3称宋明是典型汉人文人政权，审美判断不是表象的；满族进来后对美的判断是表象的，今天外在美直观能看到的都卖得贵，但晚清到民国初年收藏中素雅的东西才值钱。
-- **明朝皇帝与大臣关系**：发言者2称明朝皇帝想去江南，大臣跪在金水桥前抗议不让去，明武宗气坏了到锦衣卫打死了十几个还是不让去；到扬州要东西政府说没有，皇帝不生气，把酒席折合成银两带回去。
+## 日本历史剧《大奥》与日本文化
+- **《大奥》反响**：发言者1引出刚播完并引起很大反响的《大奥》，发言者3认为它是《大长今》以后最有影响的外国电视剧，发言者2表示赞同。
+- **《大奥》历史背景**：发言者3介绍该剧三部曲，前两部对应中国晚明到清初时段，发言者2补充后一部在明治维新之前，是一部有跨越性的历史剧。
+- **大奥含义**：发言者3解释大奥即普通话的后宫，日语中「奥」指很深的地方、屋子最里处，发言者2补充另一层意思是一般人不准进去。
+- **大奥的规矩**：发言者3指出大奥定下非常严谨的规矩，包括后宫不许进人；发言者1描述将军出场时所有人呈45度鞠躬、依次鞠躬的场面华丽。
+- **幕府将军与天皇关系**：发言者2说明天皇一直是摆设，实际权力在幕府将军，德川家康开创德川幕府后权力集中在一人手上；天皇曾因想举办活动没钱找将军要钱被拒，后以退位抗议。
+- **日本极端精神**：发言者2认为从《大奥》可看出日本文化从头到尾没变，是一种极端精神，所有事情要做到尽头；发言者3补充它是发自内心的，与中国人不同。
+- **战后经济成就**：发言者3指出日本1945年战后用30年时间成为世界第二经济强国，以绝对量计，是强国中唯一没有资源的国家。
+## 中日文化差异与日本民族精神
+- **中国中庸与日本极端**：发言者2对比中国中庸文化与日本极端精神，以家具店硬木刻云彩为例，说明中国讲究融合、走最适合的路；日本则坚持一个原则，如炮手开炮时忘记一切只记得把炮开出去即达最高境界。
+- **日本忠诚文化**：发言者3认为日本是忠诚文化的典型国度，忠诚靠具体事例体现而非说教，如《大奥》中阿福25岁进大奥当奶妈、65岁去世，40年完全出于公心做事。
+- **终身雇佣制**：发言者2指出日本跳槽率最低，终身雇佣制下缺乏竞争却仍保持高积极性，是西方经济学家不能理解的经济学奇迹。
+- **投机取巧无生存环境**：发言者3认为日本投机取巧的人没有生存环境，社会文化的鄙视非常难过；举例日本做绳子做到全日本第一的人，几年不赚钱铺市场，最终通过两边各加2%获利。
+- **日本重视死亡**：发言者2认为日本民族有寻死的潜在欲望，因岛国生存条件恶劣而对死亡不惧怕甚至有点向往；发言者3修正为日本民族不是藐视生命而是重视死亡，经济危机时身家万贯者剖腹自杀。
+- **日本豆腐厂见闻**：发言者3讲述参观日本最底层工厂，豆腐厂规定当天做当天卖，所有人夜里11:45坐好等钟，12点整一起开始工作，到四点多干完上市，无人闲聊。
+## 明朝历史与《明朝那些事》
+- **《明朝那些事》发行**：发言者3指出该书发行量排行第一，各报文学类都是第一。
+- **写明史的原因**：发言者2解释写明史因明史资料最多，历史研究有两个难点：先秦春秋没史料，明清史料太多但同一事件可能有7个不同说法，如罗生门。
+- **明朝历史特点**：发言者3指出明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变、夺门之变，皇上被瓦剌军抓起来又扶弟弟上位，构成现代版电视剧情节。
+- **朱元璋评价**：发言者2认为朱元璋从乞丐当上皇帝独此一份，刘邦好歹是亭长；朱元璋定下明朝规章制度基本无大改动，是了不起的人才；发言者3认为人的因素最大，改变时势一定出现一个人。
+- **朱元璋参加起义**：发言者2讲述朱元璋因送信被人告发，没办法只能去参加起义军，当年造反是要掉脑袋的风险事。
+- **明末市民生活**：发言者2指出明末很多真相被掩盖，市民生活轻松舒服，想去哪去哪，江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍等娱乐产品出现说明有养活自己的资本；李自成起义因陕西大规模灾荒。
+- **明末艺术**：发言者3指出明末工艺变得非常精细，日本派大量工匠来交流学习；文征明、唐寅、董其昌都是那个时期的人，画的是小桥流水，而八大山人画翻白眼是对社会愤愤不平。
+- **历史经验教训**：发言者2提出「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因历史事件发生时有背景，史书记载只是照片，而古人的生活是录像，不能套用经验。
+- **1644年北京瘟疫**：发言者2提到1644年明朝灭亡那年北京闹瘟疫，叫疙瘩瘟，今天看就是天花，曾与老师王佩奇交流认为明朝亡得蹊跷。
+- **王朝300年大限**：发言者3指出中国历史王朝300年是大限，跨过300年的只有宋朝（南北宋接上，退让大半个国土延续319年），汉朝中间隔断14年，唐朝明朝清朝都没跨过。
+## 明朝皇帝趣事与历史评价
+- **明武宗去江南**：发言者2讲述正德皇帝要去江南，大臣全跪金水桥前抗议，皇帝气坏了到锦衣卫打死十几人还是不让去。
+- **正德打秋风**：发言者2讲述正德到扬州要东西，政府说没有，皇帝不生气，让人准备酒席后说吃不了，把酒席折合成银两带回去。
+- **天启帝当木匠**：发言者3讲述天启帝干完活差大臣去卖，回来打听卖得怎么样，卖得很好成就感特大；发言者4调侃要是亲自去卖更好卖。
+- **正德被写坏的推测**：发言者2认为正德皇帝被评价为最荒淫可能因嘉靖非其亲生而是堂兄弟，嘉靖指派杨廷和等人编《明武宗实录》有偏颇；正德从江南回来在通州先停半天，派人打探京城有无埋伏，显示很有城府。
+- **正德豹房**：发言者2解释豹房其实是玩的地方，有动物园养了豹子，也有女人，但后宫也是女人，不影响其他问题。
+- **正德无后**：发言者3指出正德是明朝定论最荒淫的皇帝，没少找女人但不留种，没有生育能力，到嘉靖这拐弯。
+- **正德对宫廷外女人有兴趣**：发言者3认为正德对宫廷内女人没兴趣因禁忌太多，发言者4补充宫廷女人被训练过、太保守，民女不知他是谁所以不一样。
+- **明式家具地位**：发言者3指出天启帝当木匠从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然，皇帝下大力气做可见影响之深。
 # 关键引语与金句
-&gt; “慢慢来才是最快的方法。”
-- 发言者2在讨论日本文化中按角色做事、不夹杂小聪明时引用他人观点，说明各司其职形成合力最有效率。
-&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
-- 发言者2回应明朝兴亡经验教训能否借鉴时总结，强调历史经验不能简单套用。
-&gt; “历史它那个事儿发生的时候是有背景的……当那种情况出现的时候，你也得那么办。”
-- 发言者2解释为何不能以事后聪明评判前人，指出史书记载只是“照片”，真实生活是“录像”。
-&gt; “日本的文化跟中国的文化存在一个极大的不同……中国的文化精神是什么？是中庸。”
-- 发言者2对比中日文化差异时提出，中国讲中庸融合，日本坚持一个原则做到极致。
-&gt; “日本战后……用30年的时间成为世界第二经济强国，它不是一个偶然，它是一个必然。”
-- 发言者3谈到日本极端精神时举例，说明全民族的极端精神使资源匮乏的日本在战后迅速崛起。
-&gt; “日本人的跳槽率是最低的……每一次跳槽都是社会资源的浪费。”
-- 发言者3回应日本忠诚文化时指出，终身雇佣制下日本员工积极性仍高，跳槽率低是经济上的奇迹。
-&gt; “一个人到战场上死生多少年没死，最后积累下来经验，然后我一上战场我就知道唉敌人会往哪走，我该怎么打。天赋。”
-- 发言者2以《亮剑》李云龙为例，解释朱元璋等开国者的军事才能来自实战经验而非书本。
-&gt; “你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。”
-- 发言者3回应历史评价问题时说明，后人因能俯视历史才显得聪明，身处其中者无法看清全局。</t>
+&gt; 慢慢来才是最快的方法。
+- 回应如何理解日本文化中按角色行事、不夹杂个人小聪明的思维方式。
+&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
+- 回应明朝兴亡能否体现历史经验教训的问题。
+&gt; 历史它那个事儿发生的时候是有背景的……你不比前人聪明，你甚至可能比前人笨，当那种情况出现的时候，你也得那么办。
+- 解释为何不能简单套用历史经验教训。
+&gt; 史书上记载下来的是什么？照片。我们实际的生活，古人的生活都是录像。
+- 说明史书记载与真实历史之间的差距，回应为何很多人对历史有误解。
+&gt; 日本的文化跟中国的文化存在一个极大的不同……中国的文化精神是什么？是中庸。
+- 对比中日文化差异，以马未都家具店中硬木刻云彩为例说明中庸之道。
+&gt; 日本人的这种极端精神，使一个国家在战后这样一个不利的局面下，只需要30年的时间它进入世界第二经济强国。
+- 回应日本战后经济崛起的原因，强调其全民族极端精神的作用。
+&gt; 日本民族它不是藐视生命，它是重视死亡，它是翻着的。
+- 回应发言者2关于日本藐视生命的说法，以经济危机时身家万贯者剖腹自杀为例。
+&gt; 一个人到战场上死生多少年没死，最后积累下来经验，然后我一上战场我就知道敌人会往哪走，我该怎么打。天赋。
+- 以《亮剑》中李云龙为例，解释朱元璋这类人物的军事天赋。</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>61.9</v>
+        <v>61.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14719/3952</t>
+          <t>14719/3519</t>
         </is>
       </c>
     </row>
@@ -5790,36 +5779,38 @@
       <c r="C17" t="inlineStr">
         <is>
           <t># 就诊概况
-48岁男性患者张学恒，在成都轻工研究所从事科研工作，因上腹反复疼痛4年、近3个月加重，于消化专科就诊。医生初步判断病情复杂，需进一步检查明确诊断。
+48岁男性患者张学恒，在成都轻工研究所从事科研工作，因上腹反复疼痛4年、近3个月发作频繁，于消化专科就诊。医生初步了解病情后，建议留大便检查并预约胃镜检查，以明确有无消化道出血及进一步诊治。
 # 病史与背景
-- **现病史**：上腹疼痛4年，每年春季多发，近3个月反复发作；疼痛位于心窝部，呈烧灼感，进食冷硬食物或工作紧张时诱发；近4年出现2次黑便（分别于1年前和3个月前），均住院治疗后大便转黄；近2个月呕吐数次，呕吐物为酸味黄水样物，含当日食物；近3个月无黑便，大便黄色，小便正常，体重无明显下降。
-- **既往史**：16岁患甲肝，住院1个月治愈，肝功能正常；无手术史；偶尔口腔溃疡。
-- **过敏史**：磺胺药过敏，表现为左手红疹、瘙痒，持续约半个月。
-- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，婶婶（无血缘关系）患胃癌。
-- **个人史**：吸烟史，近期减至每日10支以内；饮酒少量，应酬时偶尔；工作紧张、经常加班熬夜。
-- **近期用药**：近期服用奥美拉唑、阿莫西林及医务室自配胃炎合剂，效果不佳。
+- **现病史**：上腹疼痛4年，每年春季多发，近3个月反复发作；疼痛位于心窝部，呈烧灼感，冷食、硬食、辛辣及工作紧张时诱发，无夜间痛醒，疼痛可忍受。
+  - 一年前及三个月前各出现一次黑便，每次持续约一个月，每日最多两次，大便形状基本正常，仅颜色改变；两次均住院治疗，住院后大便转黄。
+  - 近两个月呕吐数次，吐出酸味黄水样物，含未消化食物，多在晚上感觉胀时吐出。
+- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；无手术史。
+- **过敏史**：小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手出现红疹，持续半个月，确诊磺胺药过敏，此后不能服用磺胺药。
+- **家族史**：父亲76岁，有低血压；母亲75岁，有冠心病；婶婶（叔叔的爱人）有胃癌，患者担心自己是否患胃癌。
+- **个人史**：成都人，在成都轻工研究所从事科研工作，工作紧张，经常加班熬夜；吸烟史，以前每天一包，现限制在10支以内；偶尔饮酒，平时不喝；喝茶，一天泡两次。
+- **近期用药**：近期服用奥美拉唑、阿莫西林及医务室配制的胃炎合剂，效果不佳。
 # 诊断与检查结果
-医生未给出明确诊断结论，建议进一步检查以排除消化道出血或肿瘤可能。
+医生初步判断患者病情与工作紧张、饮食刺激有关，建议进一步检查以明确诊断。患者有两次黑便史，需明确有无消化道出血；有胃癌家族史（婶婶），虽无血缘关系，但患者有担忧。
 # 治疗方案与医嘱
-- **检查安排**：留大便检查，以明确有无出血；胃镜预约在后天进行。
-- **生活方式**：建议戒烟、少喝酒，因吸烟和饮酒对胃部疾病有不良影响；注意避免工作紧张和熬夜。
-- **复诊与陪同**：胃镜当天由爱人陪同。
-- **后续计划**：医生将向上一级张医生汇报病情后，再与患者商量下一步处理意见。
-| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
-| --- | --- | --- | --- | --- |
-| 奥美拉唑 | 未提及 | 未提及 | 口服 | 国产（武汉药厂） |
-| 阿莫西林 | 未提及 | 未提及 | 口服 | 未提及 |
-| 胃炎合剂 | 未提及 | 未提及 | 口服 | 医务室自配 |
+- **检查安排**：留大便检查以明确有无出血；预约后天做胃镜检查，患者要求后天以便爱人陪同，医生同意。
+- **生活方式**：建议戒烟、少喝酒，因吸烟饮酒可能加重胃部疾病；注意避免熬夜，因工作紧张劳累可能诱发疼痛。
+- **复诊与陪同**：胃镜活检后恰逢张大夫查房，便于进一步诊治；患者爱人后天可请假陪同。
+| 药品名称 | 用法用量 | 注意事项 |
+| --- | --- | --- |
+| 奥美拉唑 | — | — |
+| 阿莫西林 | — | — |
+| 胃炎合剂 | — | — |
 # 复诊与预警信号
-复诊时间未明确。⚠️ 需立即就医的预警症状：原文未提及。</t>
+复诊时间：后天做胃镜检查，胃镜活检后由张大夫查房。
+⚠️ 需立即就医的预警症状：原文未提及。</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>33.5</v>
+        <v>38.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8519/865</t>
+          <t>8519/1010</t>
         </is>
       </c>
     </row>
@@ -6774,46 +6765,53 @@
       <c r="C18" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决提起上诉。合议庭依法组成并公开开庭审理，围绕动产抵押权与融资租赁所有权冲突、罚息复利计算、违约金连带责任三个争议焦点展开法庭调查与辩论。经合议庭评议提出调解方案，各方均无异议，最终达成调解协议，合议庭确认并出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审案件，由最高人民法院依法组成合议庭公开开庭审理。庭审围绕三个争议焦点展开：一是抵押权与融资租赁所有权冲突问题，二是罚息、复利计算问题，三是违约金连带责任问题。各方充分发表意见后，合议庭休庭评议并提出调解方案，各方均无异议，同意签署调解协议。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国家开发银行） | 请求改判一审判决，支持其利息、罚息、复利计算方式及违约金主张 | 主张已按央行规定查询融资租赁登记系统，未发现曲靖电力公司设备存在融资租赁记录，构成善意取得；利息应计算至2018年6月13日，罚息自该日起算，复利按合同第六条第四款约定计算；依据借款合同第24条第三项，东源煤电未配合办理账户管理及柜台协议构成违约，应支付千分之一违约金 |
-| 被上诉人（云南东源电力股份有限公司、云南东源曲靖电力有限公司） | 请求驳回上诉，维持原判 | 主张已通过2015年12月2日邮件告知国开行设备存在融资租赁，国开行未尽注意义务；国开行宣布贷款提前到期未给合理期限，不符合合同约定；罚息不应作为复利计算基数，复利再计算复利无合同依据；国开行未举证证明违约行为，且未发出限期纠正通知，不符合违约金主张条件 |
-| 被上诉人（招银金融租赁有限公司） | 请求驳回上诉，维持原判 | 主张国开行在2015年办理抵押时未进行有效查询，不构成善意取得；东源煤电2012年已取得设备所有权，其出资行为系无权处分；融资租赁登记系行业指导性规范，不产生物权后果 |
+| 上诉人（国开行） | 请求撤销一审判决相关部分，改判支持其利息、罚息、复利计算主张及违约金请求 | 主张其审查义务仅限于抵押人曲靖电力公司，已尽合理审慎义务；2018年核查时曲靖电力公司名下无融资租赁登记，构成善意取得；罚息、复利计算有合同依据；东源煤电未配合办理账户管理及柜台签约手续，构成违约，应支付千分之一违约金 |
+| 被上诉人（东源电力、东源曲靖电力） | 请求驳回上诉，维持原判 | 主张国开行未在抵押时查询融资租赁登记，不构成善意取得；罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条；国开行宣布贷款提前到期未给合理期限，不符合合同约定；国开行未举证东源煤电违反柜台协议，且未发出限期纠正通知，主张违约金不符合合同约定 |
+| 被上诉人（招银租赁） | 请求驳回上诉，维持原判 | 主张国开行未在抵押时查询融资租赁登记，不构成善意取得；其2012年已取得设备所有权，国开行2015年抵押登记在后；东源煤电出资行为系无权处分；融资租赁登记系行业指导性规范，不当然产生物权后果 |
 # 举证与法庭调查
 ## 举证与质证
-- **国开行提交**：2018年9月融资租赁查询证书，证明已按央行规定查询融资租赁登记系统，未发现曲靖电力公司设备存在融资租赁记录；招银租赁质证认为该查询不符合2014年93号文要求，国开行在抵押时点未进行有效查询。
-- **国开行提交**：工商部门出资证明及权属确认材料，证明已对设备所有权尽到审慎审查义务；招银租赁质证认为工商登记公示的是出资行为而非动产所有权，东源煤电出资系无权处分。
-- **招银租赁提交**：回租设备清单（一审证据7页），载明设备名称、生产厂家，但未载明型号；国开行质证认为无法据此识别设备唯一性，且清单提示2012年3月1日，而抵押设备铭牌生产日期均在2013年以后，看不出是同一设备。
-- **招银租赁提交**：2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行质证认为该报告已载明设备出资事项，招银租赁应当知道设备出资情况。
-- **国开行提交**：2018年核查表（证据108页），证明再次核查曲靖电力公司名下仍无融资租赁登记；招银租赁质证认为该核查不符合要求。
-- **东源方提交**：2015年12月2日邮件及融资情况统计表，证明已告知国开行设备存在融资租赁；国开行质证认为邮件正文及附表均无融资租赁文字，统计表显示招银租赁抵押类型为不动产抵押，且设备名称相同但无法得出已告知的结论。
+- **国开行提交证据**：2018年9月对曲靖电力公司的融资租赁查询证书，证明其已尽审查义务；招银租赁质证认为该查询证书不符合要求，依据2014年93号文《中国人民银行关于融资租赁登记系统规定》，国开行在抵押时点未进行相应查询。
+- **国开行提交证据**：工商部门出资证明及权属证明（证据四冶合成58亿），证明已对设备所有权尽到合理审慎义务；招银租赁质证认为工商登记公示的是出资行为而非动产所有权，东源煤电出资行为系无权处分。
+- **招银租赁提交证据**：回租设备清单（一审证据7页），载明设备名称、生产厂家，但未载明型号；国开行质证认为该清单无法识别设备唯一性，且铭牌生产日期均在2013年以后，与清单提示的2012年3月1日不符。
+- **招银租赁提交证据**：2013年和2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行质证认为该报告已载明设备出资事项，招银租赁应当知道设备出资情况。
+- **国开行提交证据**：2018年核查表（证据108页），证明曲靖电力公司名下无融资租赁登记；招银租赁质证认为该核查表系诉讼中截图，不能证明抵押时点已查询。
 ## 证人/鉴定陈述
 未提及
 ## 法官询问
-- **审判员询问**：各方如何理解央行融资租赁登记的性质及法律后果？国开行认为系行业强制性规范，旨在防范金融风险；招银租赁认为系行业指导性规范，不产生物权后果；东源方认为不当然产生物权后果。
-- **审判员询问**：央行融资租赁登记系统的查询方式能否保证查询到登记结果？招银租赁称可通过公司名称或设备查询，但设备查询涉及种类物区分问题；国开行称目前只能按单位查询。
-- **审判员询问**：国开行贷款前审查是否有内部规定要求必须查询融资租赁系统，未查到结果需保留单据作为风控材料？国开行称无此规定，因无查询结果故未保留。
-- **审判员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁称不是必填项，本案设备无唯一识别码故未登记。
-- **审判员询问**：查询通知规定银行办理抵押前应查询，违反该规范会导致何种法律后果？国开行认为系基本查询义务，已对抵押人完成审慎调查；招银租赁认为银行未查询即违反行业规范，不构成善意。
-- **审判员询问**：通过其他方式获知融资租赁后是否仍需通过央行系统查询？招银租赁认为仍需查询，因央行规定出台背景即实务中大量纠纷，需确定标准衡量善意。
-- **审判员询问**：融资租赁司法解释第九条各款举证责任如何分配？招银租赁认为第一、二、四款由出租人举证，第三款由第三人（国开行）举证。
-- **审判员询问**：因不同登记机构产生登记瑕疵，各方有何意见和建议？国开行认为系统信息不完整是整体问题，建议信息整合；东源方认为系统整合有必要但非专业机构无法提供建议；招银租赁建议从立法层面统一规范，发挥行业协会作用，技术上实现登记平台统一。
+- **审判员询问**：中国人民银行征信中心融资租赁登记的性质及法律后果？国开行代理人认为系行业强制规范，招银租赁代理人认为系行业指导性规范，东源公司代理人认为不当然产生物权后果。
+- **审判员询问**：融资租赁登记系统查询方式能否保证查询到登记结果？国开行代理人称只能按单位名称查询；招银租赁代理人称可按公司名称或设备查询，但设备查询涉及种类物区分问题。
+- **审判员询问**：国开行贷款前审查是否有内部规定要求必须查询融资租赁登记，未查到需将查询单作为风控材料？国开行代理人称无此规定，因未查到结果故未保留查询单。
+- **审判员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁代理人称非必填项，本案设备无唯一标识码，故未登记。
+- **审判员询问**：查询通知规定银行办理抵押前应查询，违反该规范是否导致最高人民法院相关司法解释的适用？国开行代理人认为系基本查询义务，已对抵押人完成审慎调查；招银租赁代理人认为银行未查询即违反行业规范，应承担不利后果。
+- **审判员询问**：若通过其他渠道获知设备存在租赁，是否仍需通过央行系统查询？招银租赁代理人认为仍需查询，因央行规定出台背景即实务中大量纠纷，其他方式无法证明善意。
+- **审判员询问**：不同登记机构产生登记瑕疵时，各方有何意见和建议？国开行代理人认为系系统信息不完整、体系相互隔离所致；东源公司代理人称非专业机构，无具体建议；招银租赁代理人建议从立法层面统一规范，发挥行业协会作用，并推动登记平台统一。
 ## 争议焦点与辩论
-- **争议焦点一：动产抵押权与融资租赁所有权冲突**。国开行主张其审查义务仅限于抵押人曲靖电力公司，已按央行规定查询融资租赁登记系统，未发现融资租赁记录，且抵押登记为法定登记，构成善意取得；招银租赁主张国开行在2015年办理抵押时未进行有效查询，不构成善意，且东源煤电2012年已取得设备所有权，其出资行为系无权处分；东源方主张已通过邮件告知国开行设备存在融资租赁，国开行未尽注意义务。
-- **争议焦点二：罚息、复息计算**。国开行主张利息计算至2018年6月13日，罚息自该日起算，复利按合同第六条第四款约定计算；东源方主张国开行宣布贷款提前到期未给合理期限，不符合合同约定，且罚息不应作为复利计算基数，复利再计算复利无合同依据；招银租赁表示非合同当事人，尊重合议庭审查结果。
-- **争议焦点三：违约金连带责任**。国开行主张依据借款合同第24条第三项，东源煤电未按合同第13条、第14条配合办理账户管理及柜台协议，构成违约，应支付千分之一违约金；东源方主张国开行未举证证明违约行为，且未按合同约定发出限期纠正通知，不符合违约金主张条件。
+### 争议焦点一：抵押权与融资租赁所有权冲突
+- **国开行主张**：其审查义务仅限于抵押人曲靖电力公司，已尽合理审慎义务，2018年核查时曲靖电力公司名下无融资租赁登记，构成善意取得。
+- **招银租赁主张**：国开行未在抵押时查询融资租赁登记，不构成善意取得；其2012年已取得设备所有权，国开行2015年抵押登记在后。
+- **东源公司主张**：其2015年12月2日发送的邮件已用红色标注抵押设备与招银租赁设备名称一致，国开行作为专业金融机构应尽注意义务。
+- **国开行反驳**：邮件系贷后审查材料，非针对抵押物的告知；统计表中招银租赁栏记载的抵押类型为不动产抵押，与融资租赁不同，无法得出已告知的结论。
+### 争议焦点二：罚息、复利计算
+- **国开行主张**：利息计算至2018年6月12日合计2179万5727.08元，罚息自2018年6月13日至2019年2月19日合计4105万零579.57元，复利自2018年3月21日至2019年2月19日合计191.8206万元。
+- **东源公司主张**：罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条；国开行宣布贷款提前到期未给合理期限，不符合合同约定。
+- **国开行反驳**：合同第六条第四款明确约定罚息计收复利，且东源煤电未上诉，一审已支持罚息复利部分。
+### 争议焦点三：违约金连带责任
+- **国开行主张**：依据借款合同第24条第三项，东源煤电应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台签约手续，构成违约。
+- **东源公司主张**：国开行未举证东源煤电违反柜台协议，且未发出限期纠正通知，主张违约金不符合合同约定。
 # 庭审结果
-本案经合议庭评议，提出调解方案，各方均无异议，达成调解协议。调解方案主要内容：确认国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利共计6474.4513万元；招银租赁对涉案六项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权，招银租赁对6项设备有所有权；双方同意对案涉全部发电设备整体盘活处置，变现款各50%分配；变现款不足以清偿债务时，招银租赁未实现债权按破产重整计划预留方案实现；若司法变现不能，国开行和招银租赁放弃对案涉设备权益，由东源曲靖电力自主生产经营；一审判决第二项、第四项无争议，按判项内容在调解书中确认；一审诉讼费按一审判决执行，二审诉讼费由本院依法确定。合议庭确认调解协议，出具调解书。</t>
+本案经合议庭评议，各方当事人对调解方案均无异议，同意签署调解协议。调解方案主要内容：国开行对东源公司债权扣除已清偿本金后，利息、罚息、复利合计6474.4513万元；招银租赁对涉案六项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权，招银租赁对六项设备有所有权；双方同意整体盘活处置设备，变现款各50%，费用各担50%；若变现不足，招银租赁未实现债权按破产重整计划预留方案实现；各方对一审判决第二项、第四项无争议。合议庭将根据《中华人民共和国民事诉讼法》第97条规定出具调解书。</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>76.8</v>
+        <v>66.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30731/2888</t>
+          <t>30731/2896</t>
         </is>
       </c>
     </row>
@@ -6920,40 +6918,40 @@
       <c r="C19" t="inlineStr">
         <is>
           <t># 候选人概况与面试岗位
-本次面试为公务员结构化面试，共20分钟，回答4道题，由面试官主持、计时员计时，考生逐题作答。四道题分别考察综合分析、组织协调、应急处理和公共服务能力，考生均完成作答，无补充内容。
+本次面试为公务员结构化面试，共20分钟，回答4道题，由面试官主持、计时员计时，考生逐题作答。四道题分别考察综合分析、组织协调、应急处理和公共服务能力，考生均完成作答，面试结束。
 # 面试问答纪要
 ## 第一题（综合分析能力）
-- 题目：以骏马、风筝、陀螺与绳子的比喻，谈对做好公务员工作的启示。
-- 作答要点：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；引用曾子“吾日三省吾身”强调自我反省；单位应形成紧张、活泼、团结的风气，同事间比能力而非物质；权利与责任需平衡，建立权利清单和责任清单；以“连轴转”形容公职人员工作状态，强调责任感和成就感是动力。
+- 题目：以绳子对骏马、风筝、陀螺的不同作用为引，谈谈对做好公务员工作的启示。
+- 作答要点：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；引用曾子“吾日三省吾身”强调自我反省；单位应形成紧张、活泼、团结的风气，同事间比较能力而非物质；权利和责任需平衡，建立权利清单和责任清单；以陀螺“连轴转”比喻公务员工作，强调责任感和成就感是动力。
 ## 第二题（组织协调能力）
-- 题目：作为市政府办公室工作人员小王，负责调研本市AI企业发展状况和服务需求，为出台扶持政策提供依据。
-- 作答要点：前期准备包括补课学习AI知识、学习兄弟城市经验、查阅国务院及省厅指导意见；制定方案分客观（企业发展现状）和主观（政府服务需求）两方面；实施调研包括与企业对接、发放调查问卷、召开座谈会；管理措施通过问卷调查摸排不规范之处，以便政策规范。
+- 题目：作为市政府办公室工作人员小王，负责对本市AI相关企业进行调研，了解发展状况和服务需求，为出台扶持政策提供依据，如何完成好任务。
+- 作答要点：前期补课学习AI知识，学习兄弟城市经验，查阅国务院及省厅指导意见；制定方案分客观（企业发展现状）和主观（政府服务需求）两方面；调研涵盖市场状况、服务需求、管理措施三部分；通过企业对接、调查问卷、座谈会等方式实施；提到共享充电宝信任危机，强调AI发展需及时纠偏。
 ## 第三题（应急处理能力）
-- 题目：作为服务标兵小王，现场模拟答复记者关于管道疏通后再次堵塞的投诉。
-- 作答要点：解释管道为90年代修建、老城区改造难度大、夏季用水高峰问题集中；说明已联系维修师傅、将问题汇报上级，计划通过城市综合保障工程改善硬件；承认工作失职，请求媒体给予改进机会。
+- 题目：作为市级服务标兵小王，现场模拟答复记者关于居民投诉地下排水管道疏通后没过几天又堵上、街道污水严重、质疑标兵名不副实的情况。
+- 作答要点：解释管道为上世纪90年代修建，老城区改造难度大，夏季用水高峰问题集中；承认工作失职，请求媒体给予改进机会；表示已联系维修师傅，并将管道硬件问题汇报上级，计划通过城市综合保障工程改善。
 ## 第四题（公共服务能力）
-- 题目：从公共服务角度谈处理道路改造和雨污分流工程引发的噪音、灰尘、交通拥堵等居民不满的思路。
-- 作答要点：区分主要矛盾（时间上的需求不满足）与次要矛盾（噪音、出行、舆论）；主张坚持推进城市建设，同时采取措施减少扰民；具体措施包括督促施工方加快进度、加防噪墙、洒水降尘、建议替代路线、通过交通广播推荐路线、鼓励公交出行、增加公交班次；通过网络公告公开透明沟通，争取市民理解。
+- 题目：从公共服务角度谈谈处理道路改造和雨污分流工程引发居民不满的社会矛盾思路。
+- 作答要点：分析主要矛盾是时间上的需求不满足，次要矛盾是噪音、出行和舆论问题；提出督促施工方加快进度，使用防噪墙、洒水降尘；开辟出行便道、通过交通广播推荐路线、鼓励公交出行并增加班次；以公告形式在网络公开透明表达政府举措。
 # 能力评估
 | 评估维度 | 推荐评级 | 评估依据（具体事例） |
 | --- | --- | --- |
-| 专业/技术能力 | 未评 | 考生在第二题中主动补课学习AI知识，查阅国务院及省厅指导意见，制定调研方案，体现对专业知识的重视和快速学习能力。 |
-| 项目经验 | 未评 | 考生在第二题中提出调研步骤，包括前期准备、制定方案、实施调研，但未提及具体项目经验。 |
-| 沟通协作 | 未评 | 考生在第三题中现场模拟答复记者，解释管道问题原因，承诺解决，并请求媒体解释说明，体现沟通协调能力。 |
-| 岗位匹配度 | 未评 | 考生在第四题中从公共服务角度提出处理社会矛盾的思路，包括督促施工方加快进度、加防噪墙、洒水降尘、建议替代路线、鼓励公交出行等，符合岗位要求。 |
-| 问题解决能力 | 未评 | 考生在第四题中区分主要矛盾和次要矛盾，提出具体措施解决噪音、灰尘、交通拥堵等问题，体现问题解决能力。 |
-| 思维逻辑性 | 未评 | 考生在第一题中从自我反省、单位风气、权利与责任平衡、工作动力四方面展开论述，结构清晰，逻辑性强。 |
-| 应变能力 | 未评 | 考生在第三题中面对记者投诉，迅速解释原因、承诺解决，并请求媒体给予改进机会，体现应变能力。 |
+| 专业/技术能力 | 未评 | 考生在第二题中自述为文科生，对AI存在知识盲区，计划利用课余时间补课学习AI知识，并查阅国务院及省厅指导意见，体现主动学习意识。 |
+| 项目经验 | 未评 | 考生在第二题中提出调研方案分客观和主观两方面，涵盖市场状况、服务需求、管理措施三部分，并通过企业对接、调查问卷、座谈会等方式实施，体现组织协调经验。 |
+| 沟通协作 | 未评 | 考生在第三题中现场模拟答复记者，解释管道问题原因，承认工作失职，并请求媒体给予改进机会，体现沟通与协作意识。 |
+| 岗位匹配度 | 未评 | 考生在第四题中从公共服务角度分析主要矛盾和次要矛盾，提出加快工程进度、减少噪音灰尘、改善出行、加强宣传和沟通等措施，体现公共服务意识。 |
+| 问题解决能力 | 未评 | 考生在第三题中提出已联系维修师傅，并将管道硬件问题汇报上级，计划通过城市综合保障工程改善，体现问题解决思路。 |
+| 思维逻辑性 | 未评 | 考生在第一题中从绳子对骏马、风筝、陀螺的不同作用引申到公务员工作的启示，结构清晰，逻辑连贯。 |
+| 应变能力 | 未评 | 考生在第三题中面对记者投诉，现场模拟答复，解释原因并承认失职，体现应变能力。 |
 # 综合素质
-- **突出亮点**：考生在第三题中主动承认工作失职，并请求媒体给予改进机会，体现了诚恳态度和担当意识。</t>
+- **突出亮点**：考生在第三题中主动承认工作失职，并请求媒体给予改进机会，体现责任担当；在第二题中提出通过企业对接、调查问卷、座谈会等多种方式收集信息，方法具体可行。</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>37.4</v>
+        <v>41.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5808/1443</t>
+          <t>5808/1546</t>
         </is>
       </c>
     </row>
@@ -7022,81 +7020,96 @@
       <c r="C20" t="inlineStr">
         <is>
           <t># 参观概况
-本次参观围绕故宫中轴线及东西六宫展开，由主讲人带领观众依次游览午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、御花园等主要景点，全程穿插历史典故与建筑功能讲解。讲解从午门“明三暗五”的门洞规制讲起，涵盖太和殿举行登基、册封大典的用途，乾清宫牌匾后藏立储诏书的秘密，以及珍宝馆内九龙壁的修复故事等。游览过程中，主讲人同步介绍了故宫内七个免费盖章点及各店印章差异，并推荐了紫禁城100、文创雪糕等特色产品。行程最后，主讲人依据不同时间安排总结出三条游览路线，分别适合全天、半天及短时游览，并建议早起排队、进门后先沿中轴线错峰参观。
+本次参观为故宫博物院一日深度游览，由导游全程讲解，围绕中轴线及东西两路展开，覆盖午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、御花园等主要景点，全程穿插历史典故与建筑特色讲解。游览以午门检票入场为起点，导游依次介绍各殿功能与规制，如午门“明三暗五”结构、太和殿大典用途、乾清宫立储诏书秘密、珍宝馆乾隆养老院布局等；同时沿途标注七处免费盖章点及文创购买规则，并推荐三条不同时长的游览路线。整体过程从早间排队错峰开始，至神武门出宫结束，形成一条完整的故宫保姆级游览攻略。
 # 核心看点与讲解
-- **午门**：故宫检票入口，明朝皇帝在此杖打犯错大臣，清朝皇帝在此举行颁朔之礼。门洞为明三暗五结构，中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，两侧门走皇亲国戚和文武百官。
-- **太和门广场**：眼前有五座金水桥，中间桥供皇帝行走，挨着中间的两座桥供黄金国器通行，最边上的桥供文武百官行走。
-- **太和门**：明朝皇帝在此御门听政，即上朝的地方。门口铜狮为故宫六对铜狮中最大的一对，脚踩寰宇象征权力，不建议站在狮子底下合影。
-- **太和殿**：即金銮殿，但并非皇帝上朝之处，而是举行盛大典礼的地方，如皇帝登基、皇后册封。文武百官在太和殿广场向皇帝高呼万岁，站位遵循文东武西原则。西侧弘义阁为皇帝银库，东侧体仁阁为缎库。
+- **午门**：排队检票处，明朝皇帝在此杖打犯错大臣，清朝皇帝在此举行颁朔之礼。门洞呈“明三暗五”结构，正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次；两侧门走皇亲国戚和文武百官。
+- **太和门广场**：眼前有五座金水桥，中间桥供皇帝行走，挨着中间的两座桥供黄金国器行走，文武百官走最边上的桥。
+- **太和门**：明朝皇帝在此御门听政（上朝的地方），门口铜狮子是故宫六对铜狮中最大的一对，脚踩寰宇象征权力，不建议站在狮子底下合影。
+- **太和殿**：即金銮殿，但并非上朝之地，而是举行盛大典礼的地方，如皇帝登基、皇后册封；文武百官在太和殿广场向皇帝喊“吾皇万岁万岁万万岁”，站位遵循“文东武西”——文官站东边，武官站西边。西边弘义阁是皇帝的银库，东边体仁阁是缎库。
 - **中和殿**：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再前往太和殿。
-- **保和殿**：自乾隆五十四年起为科举考试殿试考场。东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》现场盖章，各店印章不同，购买后不能去其他店铺盖章，汉字馆印章数量最多。
-- **乾清门**：过了此门即后宫区域，皇帝在此上早朝。东边九卿直房为等级高的大臣等待召见之处，西边为军机处。门口铜狮耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
-- **乾清宫**：皇帝平时睡觉的地方，内有27张龙床，据说是为防止刺客找到皇帝位置。牌匾「正大光明」后藏皇帝立储诏书，皇帝写两份诏书，驾崩后对比验证是否被动过手脚。门口有铜鹤铜龟，旁边设江山社稷金殿，为紫禁城最小宫殿，提醒皇帝将江山社稷放在第一位。
+- **保和殿**：从乾隆五十四年开始作为科举考试殿试的考场；东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》并现场盖章，购买后不能去其他店铺盖章，据说汉字馆印章数量最多。
+- **乾清门**：过了此门即后宫区域，皇帝在此上早朝；东边九卿直房是等级高的大臣等待皇帝召见之处，西边是军机处。门口两尊狮子耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
+- **乾清宫**：皇帝平时睡觉的地方，内有27张龙床，据说是为防止刺客找到皇帝位置；牌匾“正大光明”后藏皇帝立储诏书，皇帝写两份诏书，驾崩后取出对比以防被动手脚。门口有铜鹤与铜龟，旁边有社稷江山金殿，是紫禁城里最小的宫殿，提醒皇帝把江山社稷放在第一位。
 - **交泰殿**：内放25块传国玉玺。
-- **坤宁宫**：皇后居所，明朝所有皇后都住于此。东北角文创店有5枚免费印章。
-- **储秀宫**：慈禧住了20多年的地方，现为慈禧五十大寿时期原状陈列，慈禧因儿子在此出生而喜欢此处。旁边文创店有3枚免费印章。
-- **翊坤宫与永寿宫**：翊坤宫和永寿宫往南走，永寿宫西边为太极殿，是东西六宫中唯一被称为殿的宫殿。
-- **慈宁宫与寿康宫**：慈宁宫为康熙给奶奶孝庄皇太后修建的养老院，旁边寿康宫为甄嬛居住之处。
+- **坤宁宫**：皇后住所，明朝所有皇后都住于此；东北角文创店有5枚免费印章。
+- **储秀宫**：慈禧住了20多年的地方，现为慈禧五十大寿时期原状陈列，慈禧儿子在此出生；旁边文创店有3枚免费印章。
+- **翊坤宫与永寿宫**：翊坤宫和永寿宫位于储秀宫以南，永寿宫西边是东西六宫中唯一被称为殿的太极殿。
+- **慈宁宫与寿康宫**：慈宁宫是康熙给奶奶孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住之处。
 - **冰窖书吧**：内有3枚免费印章，印章造型有批折子的感觉。
-- **断虹桥**：网红打卡地，桥上有形态各异的石狮子，最有名的为武当狮。
-- **武英殿**：后改为陶瓷馆，目前关闭状态，只能在门口观看。
-- **文华殿**：位于东边，与西边武英殿对应文东武西，参观时未开放，据说有展览。
-- **箭亭**：清朝皇帝及子孙练习骑马射箭的地方，旁边商店可购买文创雪糕。
+- **断虹桥**：网红打卡地，桥上有形态各异的石狮子，最有名的是“武当狮”。
+- **武英殿**：后改为陶瓷馆，目前关闭状态，只能在门口看看。
+- **文华殿**：位于东边，与西边武英殿对应“文东武西”，参观时未开放，据说现有一个展览。
+- **箭亭**：清朝皇帝及其子孙练习骑马射箭的地方，旁边商店可购买文创雪糕。
 - **钟表馆**：展示那个年代的钟表造型。
-- **珍宝馆**：门口有我国现存三座古代九龙壁之一，左边数第三条白色龙下边有一块木头，据说是当年烧制琉璃砖瓦弄坏后工匠为保命用木头刷白漆以假乱真。珍宝馆并非单独展厅，院子周围屋子均可参观，游客众多，尤其看凤冠需挤进去。此处为宁寿全宫，是乾隆给自己修建的养老院，乾隆退休后未放权仍照常上朝。皇极殿为1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后为乐寿堂，是故宫内唯一能进去参观的皇家寝室，有二龙仙楼设计。再往后为珍妃井，当年慈禧把珍妃丢进去，井口石为后放，珍妃并非从那个小眼进去。出口右手边商店有3枚免费印章。
-- **东筒子夹道**：长长的夹道，拍照出片，沿路往南拐弯到延禧宫。
-- **景仁宫**：当年甄嬛被封熹妃时居住，珍妃也住过。
-- **御花园**：内有钦安殿，供奉真武大帝，紫禁城靠山景山从天上看酷似闭目盘坐人像，有人说该造型就是真武大帝。
-- **神武门**：故宫北门，出门左手边有两个盖章点，角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
+- **珍宝馆**：强烈建议参观，门口有我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据说是当年烧制琉璃砖瓦弄坏后工匠为保命用木头刷白漆以假乱真。珍宝馆并非单独展厅，院子周围屋子都可参观，游客多，尤其看凤冠需挤进去。此处即宁寿全宫，是乾隆给自己修建的养老院，乾隆退休后未放权仍每天上朝办公；皇极殿1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后为乐寿堂，是故宫里唯一能进去参观的皇家寝室，有二龙戏珠设计；再往后是当年慈禧把珍妃丢进去的珍妃井，井口石并非珍妃被丢入之处。珍宝馆出口右手边商店有3枚免费印章。
+- **东筒子夹道**：长长的夹道，拍照非常出片。
+- **延禧宫与景仁宫**：延禧宫为网红打卡地，旁边景仁宫是当年甄嬛被封为熹妃时住的，珍妃也住过。
+- **御花园**：内有钦安殿，供奉真武大帝；紫禁城靠山景山从天上看酷似闭目盘坐的人像，有人说该造型就是钦安殿供奉的真武大帝。
+- **神武门**：故宫紫禁城北门，游览终点；出门左手边有两个盖章点——角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
 # 互动与体验
-- **盖章体验**：故宫内共设有七个免费盖章点，各店印章图案不同，购买《紫禁城100》后不能跨店盖章，需自行取舍。具体分布为：保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫边文创店3枚、冰窖书吧3枚、珍宝馆出口商店3枚、神武门外角楼咖啡2枚、故宫文创2枚。
-  - **汉字馆**：位于保和殿东北角，提供4枚免费印章，可现场购买《紫禁城100》并盖章，据称印章数量为各店最多，盖完后可选择邮寄到家或自行携带。
-  - **坤宁宫文创店**：位于坤宁宫东北角，提供5枚免费印章。
-  - **储秀宫文创店**：位于储秀宫边上，提供3枚免费印章。
-  - **冰窖书吧**：提供3枚免费印章，主讲人评价印章造型好，盖章时有批折子的感觉，并在此购买了冰溪图。
-  - **珍宝馆出口商店**：位于珍宝馆出口右手边，提供3枚免费印章。
-  - **神武门外盖章点**：出门左手边有两个盖章点，角楼咖啡2枚、故宫文创2枚。
-- **文创雪糕**：箭亭旁边的商店可购买文创雪糕，主讲人邀请观众在评论区猜雪糕造型对应的历史人物。
-- **拍照打卡**：太和门门口铜狮为故宫六对铜狮中最大的一对，主讲人建议单独给铜狮拍照，不建议站在狮子下方合影，因大爪子在头顶不美观；东筒子夹道拍照非常出片，是很多游客喜欢的打卡地。
-- **互动提问**：主讲人在讲解中多次向观众提问互动，包括文武百官的站位方式、断虹桥石狮中武当狮的位置、九龙壁白色龙下木块的秘密是否被皇帝发现、御花园与和珅后花园的偏好选择等，欢迎观众在评论区分享答案。
-- **个人感受**：主讲人形容珍宝馆内宝贝令人惊艳，每样都能让人说出常用感叹词，但游客太多，尤其是看凤冠的区域，没点技术挤不进去；钟表馆的钟表造型出乎意料，感叹「真是开了眼了」；在冰窖书吧盖章时感觉像批折子。
+- **排队检票**：导游建议早点过来排队，排队检票处即午门，可借此观察午门外观。
+- **午门门洞观察**：从正面看午门有三个门洞，进门后可见变成五个门洞，即“明三暗五”结构；导游提示中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名可出一次。
+- **太和门铜狮子合影提醒**：门口铜狮子为故宫六对铜狮中最大的一对，造型威武、脚踩寰宇，导游建议不要站在狮子底下合影，因大爪子正好盖在头顶，单独给狮子拍照即可。
+- **中和殿与保和殿参观**：中和殿为盛大典礼时皇帝的休息室；保和殿自乾隆五十四年起为殿试考场，导游以“弹幕走一波前途无量”互动祝福观众。
+- **汉字馆盖章体验**：保和殿东北角汉字馆有4枚免费印章，可购买《紫禁城100》由工作人员现场盖章；导游形容盖章“真是盖了帽了”，并提及故宫不止一处可买此书，但每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；据说汉字馆印章数量最多，盖完后可选择邮寄到家或自行带走。
+- **乾清宫参观提示**：可往殿内看“正大光明”牌匾，牌匾后藏皇帝立储诏书；门口有铜鹤与铜龟，旁边还有紫禁城里最小的宫殿——社稷江山金殿。
+- **坤宁宫文创店盖章**：坤宁宫东北角文创店有5枚免费印章，导游提醒别错过。
+- **储秀宫参观与盖章**：储秀宫为慈禧居住20多年的地方，现为慈禧五十大寿时期原状陈列；其子在此出生；旁边文创店有3枚免费印章。
+- **慈宁宫与寿康宫打卡**：慈宁宫为康熙给奶奶孝庄皇太后修建的养老院，旁边寿康宫为甄嬛居住地，导游提醒喜欢看《甄嬛传》的游客可到此打卡。
+- **冰窖书吧盖章**：冰窖书吧内有3枚免费印章，导游称印章造型好，盖章时有批折子的感觉；其本人因已买《紫禁城100》，在此购买了冰嬉图。
+- **断虹桥找狮子**：断虹桥上有形态各异的石狮子，最有名的是“捂裆狮”，导游邀请游客找一找它在哪。
+- **武英殿与文华殿现状**：武英殿改为陶瓷馆但目前关闭，只能在门口看看；文华殿导游去时未开，据说现有一个展览，感兴趣可去看。
+- **箭亭文创雪糕**：箭亭为清朝皇帝及子孙练习骑马射箭之处，旁边商店可买到文创雪糕，导游提问雪糕造型是谁，欢迎在评论区分享。
+- **钟表馆参观**：导游带看钟表馆，感叹“不来不知道钟表竟然还有这种造型，真是开了眼了”。
+- **九龙壁找木头龙**：珍宝馆门口为我国现存三座古代九龙壁之一，左边数第三条白色龙下边有一块明显不同的琉璃，实为木头刷白漆，导游讲述工匠烧坏琉璃后以假乱真的典故，并提问“当时皇上究竟有没有发现这个小细节”。
+- **珍宝馆参观体验**：珍宝馆并非单独展厅，院子周围屋子都值得进去看；导游称每样宝贝都能让人说出感叹词，但游客太多，尤其是看凤冠的“没点技术还真挤不进去”。
+- **乐寿堂参观**：乐寿堂为故宫里唯一能进去参观的皇家寝室，可看到二龙戏珠设计，导游提示会联想到恭王府和珅的卧室。
+- **珍妃井说明**：珍妃井为当年慈禧丢珍妃之处，导游澄清井口上方现为井口石，珍妃并非从那个小眼进去的。
+- **珍宝馆出口商店盖章**：珍宝馆出口右手边商店有3枚免费印章，导游提醒收集印章者别漏了。
+- **东筒子夹道拍照**：东筒子夹道拍照非常出片，是很多小姐姐喜欢来的地方。
+- **延禧宫与景仁宫打卡**：延禧宫为网红打卡地，旁边景仁宫为甄嬛被封熹妃时所住，珍妃也住过。
+- **御花园与钦安殿**：御花园内有钦安殿，供奉真武大帝；导游提及紫禁城靠山景山从天上看酷似闭目盘坐人像，有人说造型就是真武大帝。
+- **神武门出口盖章**：神武门出口左手边有两个盖章点，角楼咖啡有2枚免费印章，故宫文创也有2枚免费印章。
+- **三条游览路线选择**：导游总结三条路线供游客按自身情况选择——第一条走完视频内所有景点，适合打算待一整天的游客，建议早起排队、进门往里冲以错开旅游团，导游本人一天走了3万步；第二条沿中轴线看完坤宁宫后去景仁宫、延禧宫，再逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天；第三条沿中轴线看完坤宁宫后去储秀宫，出来去御花园，从神武门出，约2小时，最省力。
+- **盖章点汇总**：导游标注了七个可免费盖章的位置，供有需要的游客截图保存。
 # 收获与建议
 ## 择时与排队
 - **早起错峰**：建议早起排队，一进门就沿中轴线往里冲，可错开大批旅游团人群；等大部队到达时，已在人少时逛完最重要的几个景点。
-- **体力预期**：走完全部景点的全天路线，一天约走3万步，游览过程中需适当休息和补充水分。
+- **全天体力预期**：走完所有景点的路线一天约走3万步，游览过程中需适当休息和补充水分。
 ## 路线选择
-- **全天路线**：走完视频内提到的所有景点，适合打算在故宫待上一整天的游客。
-- **半天路线**：进门沿中轴线往后走，看完坤宁宫后去景仁宫和延禧宫，接着逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天时间逛完。
-- **省力路线**：进门沿中轴线往后走，看完坤宁宫后去储秀宫，出来去御花园，从神武门出，约2小时逛完，最省力，适合时间有限、不想走太多路的游客。
-## 盖章点
-- **保和殿东北角汉字馆**：4枚免费印章，可购买《紫禁城100》并现场盖章，据说是故宫里印章数量最多的店。
+- **第一条路线（全天）**：走完视频内提到的所有景点，适合打算在故宫待上一整天的游客；进门后沿中轴线往后走，一天约3万步。
+- **第二条路线（半天）**：进门沿中轴线往后走，看完坤宁宫后去景仁宫和延禧宫，接着逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天逛完。
+- **第三条路线（约2小时）**：进门沿中轴线往后走，看完坤宁宫后去储秀宫，出来去御花园，从神武门出；最省力，适合时间有限、不想走太多路的游客。
+## 盖章点汇总
+- **保和殿东北角汉字馆**：4枚免费印章；可购买《紫禁城100》并现场盖章，据称此处印章数量最多。
 - **坤宁宫东北角文创店**：5枚免费印章。
-- **储秀宫边文创店**：3枚免费印章。
+- **储秀宫文创店**：3枚免费印章。
 - **冰窖书吧**：3枚免费印章，印章造型好，盖章时有批折子的感觉。
-- **珍宝馆出口商店**：3枚免费印章，位置在珍宝馆出口右手边往里走。
-- **神武门外角楼咖啡**：2枚免费印章。
-- **神武门外故宫文创**：2枚免费印章。
-- **跨店限制**：故宫里不止一处可买到《紫禁城100》，每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；可选择邮寄到家或自己带走。
+- **珍宝馆出口商店**：3枚免费印章。
+- **神武门出口左手边角楼咖啡**：2枚免费印章。
+- **神武门出口故宫文创**：2枚免费印章。
+- **《紫禁城100》购买规则**：故宫不止一处可买到，但每家店印章不同；购买后不能去其他店铺盖章，需有所取舍；盖完后可选择邮寄到家或自行携带。
 ## 注意事项
-- **午门通行规则**：午门中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次；旁边两门走皇亲国戚和文武百官。
-- **太和门铜狮**：门口铜狮是故宫六对铜狮中最大的一对，造型威武、脚踩寰宇象征权力，不建议站其下方合影（大爪子会盖在头顶），单独拍照即可。
-- **太和殿非上朝处**：太和殿是举行盛大典礼的地方（皇帝登基、皇后册封），不是皇帝上朝的地方；百官站位为文东武西。
-- **乾清宫立储诏书**：牌匾「正大光明」后藏皇帝立储诏书，皇帝写两份，驾崩后对比验证是否被动过手脚。
-- **珍妃井**：井口上方现为井口石，珍妃并非从那个小眼进去的。
-- **陶瓷馆状态**：武英殿改成的陶瓷馆目前关闭，只能在门口看看。
-- **文华殿展览**：主讲人去时文华殿未开，据说现有一个展览，感兴趣可前往。
-- **珍宝馆人流**：珍宝馆内游客非常多，尤其是看凤冠的区域，没点技术挤不进去。
-- **九龙壁细节**：九龙壁左边数第三条白龙下方有一块木头，是当年烧制琉璃砖瓦弄坏后，工匠为保命用木头刷白漆以假乱真。
-## 饮食与休息
-- **冰窖书吧**：可在此休息，内有3枚免费印章，也可购买文创产品（主讲人购买了冰溪图）。</t>
+- **午门正门通行规则**：中间正门仅供皇帝行走；皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，旁边两门走皇亲国戚和文武百官。
+- **金水桥通行规则**：想体验皇帝待遇走中间桥，皇亲国戚走挨着中间的两座桥，文武百官走最边上的桥。
+- **太和门铜狮子**：不建议站在铜狮子下合影，其大爪子正好盖在头顶，建议单独给狮子拍照。
+- **太和殿非上朝处**：太和殿是举行盛大典礼的地方（皇帝登基、皇后册封），上朝在太和门（明朝御门听政）和乾清门。
+- **珍宝馆参观**：珍宝馆不是单独展厅，院子周围屋子都要进去看；游客多，尤其看凤冠需挤进去。
+- **珍妃井**：井口上方现放的是井口石，珍妃并非从那个小眼进去的。
+- **陶瓷馆状态**：武英殿改为陶瓷馆，目前关闭，只能在门口看看。
+- **文华殿展览**：导游去时未开，据称现有一个展览，感兴趣可前往。
+- **断虹桥打卡**：桥上石狮子形态各异，最有名的是“捂裆狮”，可自行寻找。
+- **文创雪糕**：箭亭旁商店可买到文创雪糕。
+- **东筒子夹道**：拍照非常出片，适合打卡。
+- **御花园对比**：有游客认为御花园比不过和珅家的后花园。</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>39.2</v>
+        <v>44.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4497/3811</t>
+          <t>4497/4820</t>
         </is>
       </c>
     </row>
@@ -7241,65 +7254,63 @@
       <c r="C21" t="inlineStr">
         <is>
           <t># 访谈概况
-本次访谈以留守老人养老问题为核心议题，由主持人实地走访农村与城市社区，访问村政府、民政局干部、农村留守老人及城市社区养老社工，了解养老现状、政策执行情况与社工服务困境。调研数据显示，65.5%的老人子女长期不在身边、无奈独居，仅26.8%的老人与子女同住；独居老人普遍存在无人照料、就医困难、生活孤独等问题，并出现黑龙江绥滨独居老人因寂寞报警、上海及杭州各一名67岁独居老人去世多日才被发现的案例。农村方面，受访干部介绍了五保户分散供养每月475元生活费加护理补贴、残疾人一级二级纳入最低生活保障（标准为160、270、380元三档）、60岁以上农村老年人每月118元养老金等政策，同时反映养老设施运营经费后续无支持、地方财政困难的问题。城市方面，社工介绍了志愿者一对一帮扶、积分兑换礼品、小手拉大手、送春联、做月饼等活动及养老服务中心建设情况，并反映社工工资低、流动性大、专业能力欠缺、项目资金不稳定等困境。整体反馈基调以呈现问题与困境为主，受访者同时提出了加强专业陪伴、倡导子女联系、丰富文化生活、建设固定养老设施并保障持续运营经费等改善建议。
+本次访谈以实地走访与对话形式展开，围绕农村与城市留守老人养老问题，访问了村政府/民政局干部、农村留守老人、城市社区社工等对象，旨在了解留守老人养老现状、政策困境及社区服务模式。访谈覆盖三大议题：留守老人生活现状与困境、农村养老政策执行情况、城市社区养老模式探索。整体反馈基调为：留守老人群体规模庞大，存在无人照料、就医困难、孤独寂寞等突出问题；农村养老政策保障水平有限、设施运营经费不足；城市社区志愿者制度与养老服务中心有一定成效，但社工行业面临工资低、人员流失、专业欠缺等困境。
 # 核心反馈
-## 农村留守老人（村政府/民政局干部视角）
-- **独居规模**：2021年公安数据显示当地73万多老人，占17.8%左右，预计还会增加；因1962—1965年职工档案出生的人特别多、去年开始退休，老龄化程度会越来越严重，估计目前至少有两三万留守老人。
-- **经济困难**：当地经济不太发达，老人生病、锻炼等首先面临经济困难；子女不在身边，一旦生病住院比较麻烦。
-- **娱乐方式少**：老人只能坐在一起聊聊天、打打牌。
-- **养老设施运营经费无后续支持**：之前探索过在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但“不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的”。
-- **五保户供养标准**：集中供养的五保户自愿到敬老院，生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养的五保户每月发475元生活费，另有护理补贴。
-- **低保与残疾人保障**：残疾人一级二级按国家政策纳入最低生活保障，有160、270、380元三个标准，视家庭状况制定，最起码保证最低生活保障。
-- **农村养老金偏低**：60岁以上农村老年人每月118元，干部认为还应提高，“农村的养老金跟工人的养老金待遇完全一样，但现在的老年人公平”——因60年代的人结婚、砍树、杀猪都要交费，与工人待遇差距不公平。
-## 农村留守老人（受访老人视角）
-- **孤独寂寞**：黑龙江绥滨一位独居老奶奶因一个人在家太寂寞，报警谎称有人敲门，只为找人说说话。
-- **独居风险**：上海一名67岁独居老人去世多日，家中溢出刺鼻气味才被邻居发现；杭州一名67岁独居老人同样去世数天后才被发现。
-- **子女外出务工**：老人反映村里80%年轻人都外出打工，“形是的呀没得人亲好”，生病时无人照看。
-- **日常劳作**：老人仍从事喂鱼、喂猪、卖货等劳动，有老人养了七八个猪。
-## 城市社区养老社工
-- **志愿者一对一帮扶**：社区给志愿者划分一对一帮扶对象，如老人住在志愿者家楼下，志愿者天天去看望，老人身体不好时天天送菜；通过定期表彰、志愿者积分兑换（年底可到雷锋超市兑换礼品）激励志愿者长期坚持。
-- **发掘中年志愿者**：在原有志愿者基础上发掘偏中年一点的志愿者；今年开展“小手拉大手”活动，从儿童青少年入手，拉动家长加入志愿者队伍。
-- **社区活动**：周四准备开展送春联活动，邀请书法老师写对联，由孩子们上门送给老人家；去年中秋节开展做月饼活动，还做过百家宴，让老人感觉社区就是大家庭。
-- **2023年目标**：此前每次活动都由社区策划开展，2023年目标是家长自己组织活动，社区作为协助者。
-- **养老服务中心**：每个社区都要成立养老服务中心，提供理疗类活动，另有按摩、老年大学、心理咨询等服务。
-- **心理问题老人案例**：曾帮助一位与邻里关系不和谐、半夜摔门的老人，志愿者上门服务但老人抗拒，“我不需要你的关心”，觉得周围人都是陌生的、没有关心他的人，内心有仇恨式情绪；经社工日复一日关心照料，现在与邻里关系好转，能接受意见，但老人仍打电话说“寂寞空虚，得不到人关注一样”。
-- **社工工资低、流动性大**：社工行业迅速发展但工资比较低，影响就业率，“基本上很多同学就没做多久，基本上都垮了，可能不超过一年”。
-- **社工专业能力欠缺**：很多社工并非社工专业出身，“可能也就是图一个，周末玩玩”，专业上很欠缺。
-- **项目资金不稳定**：社工服务领域多（留守儿童、留守老人等），专注力不集中；项目需花钱购买服务，不一定今年服务了明年又能服务，要看领导能否争取到项目；一年服务成效不明显，资金拨不下来项目就结束，但服务成效不一定达到。
-- **社工供给不足**：每个街道和乡镇派两名社工驻点，主要围绕老人、小孩服务，但“很难能够走下来”；政府和社区资金有限，难以承担长期专业社工服务费用，大量社工迫于生计转行，阻碍行业长期发展。
+## 农村留守老人
+- **独居比例高**：据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边，无奈独居，仅26.8%的老人与子女同住。
+- **无人照料与就医困难**：独居老人不同程度存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自一人在家中发生意外。
+- **孤独寂寞**：黑龙江绥滨一位独居老奶奶因一个人在家太寂寞，报警谎称有人敲门，只为找个人聊聊天。
+- **独居去世多日才被发现**：上海一名67岁独居老人在家中去世，多日后家中溢出刺鼻气味才被邻居发现；杭州一小区一名67岁独居老人同样在去世数天后才被发现。
+- **老龄化趋势加剧**：发言人2从公安了解到的数据，2021年73万多老人中17.8%左右可能独居，以后可能还会增加；1962年到1965年职工档案出生的人特别多，去年开始退休，过了几年老龄化程度会越来越严重。
+- **经济困难**：当地经济不太发达，生病、锻炼等面临经济困难；子女不在身边，一旦生病住院比较麻烦。
+- **娱乐方式少**：老人娱乐方式少，只能坐在一起聊聊天、打打牌。
+- **养老设施运营经费无后续支持**：之前探索过在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但不是一次性投入，地方财政困难，运营经费后续没有支持。
+- **农村养老金偏低**：每个60岁以上农村老年人每月118元，还要提高一点；农村养老金与工人养老金待遇完全一样，但现在的老年人不公平——60年代的人结婚、砍树要交砍伐金，杀猪要交屠宰税。
+## 村政府/民政局干部
+- **五保户供养标准**：三无人员（无收入来源、无法定赡养人和劳动能力）分集中供养和分散供养；集中供养将生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养五保户每月发475元生活费，另有护理补贴。
+- **低保标准分三档**：残疾人一、二级按国家政策纳入最低生活保障，有160、270、380元三个标准，按家庭状况制定，最起码保证最低生活保障。
+- **每月上门走访**：靠村支两委、志愿者尽量敲门串门宣传政策、搞卫生；每月开一次党员组织会，上午开会，下午搞活动或清洁大扫除，到孤寡老人、留守老人家里走一圈。
+- **上门服务不统一**：所有上门服务的都上门、入户签约的只有一个，有的一个都没有。
+- **改善建议**：请专业施工人进行陪伴；倡导在外务工子女多联系；丰富文化生活、增加娱乐方式；希望老年协会专项执行、专门建养老设施，有固定场地，定期有施工人员或宣传板报、健康知识讲座，并给持续运营经费——不只考虑建设，还要考虑后续持续运营。
+## 城市社区社工
+- **志愿者一对一帮扶**：社区给志愿者划分一对一帮扶，志愿者发现老人住在自家楼下，经过家门口上下楼时天天去看；老人身体不好时天天送菜，定期表彰或志愿者积分兑换，年底可到雷锋超市兑换礼品，让志愿者长期坚持。
+- **发掘中年志愿者**：在原有志愿者基础上发掘一批偏中年一点的志愿者；今年做了小手拉大手活动，从儿童青少年入手，拉动家长加入。
+- **送春联活动**：这周四准备开展送春联活动，邀请书法老师写对联，让孩子们上门给老人家送对联。
+- **中秋做月饼与百家宴**：去年中秋节开展做月饼活动，还做过百家宴，让大家感觉社区就是一个大家庭。
+- **2023年目标**：之前每次活动都是社区策划开展，2023年目标是家长自己组织，社区作为协助者。
+- **养老服务中心**：每个社区成立养老服务中心，提供理疗类活动、按摩、老年大学、心理咨询等服务。
+- **心理问题老人案例**：一位老人心理上出现很大问题，与邻里关系处理不和谐、半夜摔门；社区派志愿者上门，但心理问题不是仅上门能解决的，老人出现抗拒，觉得周围人都是陌生的、没有关心他的人，不接受任何人的建议；经社工日复一日关心照料，现在与邻里关系还算好了，能理解一些、接受一些意见，今天还给社工打来电话说寂寞空虚、得不到人关注。
+- **社工工资低、流失严重**：社工行业迅速发展但工资比较低，影响就业率，很多同学做没多久就垮了，不超过一年就转行。
+- **社工专业欠缺**：很多社工并不是学社工专业出来的，可能图周末玩玩，专业上很欠缺。
+- **项目资金不稳定**：服务需要花钱购买，不一定今年服务了明年又能服务，要看领导能否争取到项目；一年服务成效不明显，资金拨不下来项目就结束，但服务成效不一定达到；整个湖南省这么大，一个街道要花十来万块钱，省里还是拨了钱的。
+- **社工专注力分散**：长沙社工机构做的领域比较多，这次做留守儿童、下次做留守老人，专注力不在一个点上。
 # 关键洞察与建议
-## 农村养老现状与政策执行
-- **独居比例高**：2021年社区居家养老现状与未来趋势报告显示，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住；由此判断，独居已成为农村老人主要居住形态，无人照料、就医困难是普遍风险。
-- **独居意外案例**：黑龙江绥滨一位独居老奶奶因寂寞报警称有人敲门，民警上门后她承认是想找人聊天；上海、杭州各有一名67岁独居老人去世多日才被邻居发现——独居老人缺乏日常照应与紧急发现机制。
-- **农村老人自述**：受访老人反映子女外出打工后无人陪伴，村中60岁以上老人多，年轻人基本外出；有老人提到自己仍要喂鱼、喂猪、干农活，生活孤独且劳作负担重。
-- **老龄化趋势**：据公安数据，2021年当地73万多老人、约占17.8%，且1962至1965年职工档案出生者去年开始退休，预计老龄化程度会越来越严重——据此判断，当地养老压力将逐年加大。
-- **五保户供养标准**：集中供养的五保户由敬老院接收，生活护理补贴直接发给护理人员、生活费直接发给敬老院；分散供养五保户每月发475元生活费加护理补贴，另有食补电补合计约600来元，基本能满足农村生活但无余裕。
-- **残疾人低保标准**：一级二级残疾人按国家政策纳入最低生活保障，分160、270、380元三档，按家庭状况确定，至少保证最低生活保障。
-- **农村养老金**：60岁以上农村老年人每月118元，受访者认为农村养老金与工人养老金待遇应完全一样，现在的老年人应得到公平对待。
-- **养老设施运营困境**：此前探索过在农村建养老公共设施，提供日托、休闲娱乐、沟通交友场地，但这不是一次性投入，地方财政困难，运营经费后续没有支持——据此判断，设施建设易、持续运营难是农村养老的突出瓶颈。
-- **村两委日常帮扶**：靠村支两委和志愿者上门串门、宣传政策、搞卫生，每月开一次党员组织会，上午开会、下午到孤寡老人和留守老人家里走一圈搞大扫除。
-## 城市社区养老经验与社工困境
-- **志愿者一对一帮扶**：社区为志愿者划分一对一帮扶对象，如志愿者发现老人住在自家楼下，上下楼时天天去看望，老人身体不好时天天送菜；通过定期表彰和志愿者积分兑换（年底可在雷锋超市兑换礼品）激励志愿者长期坚持。
-- **志愿者队伍拓展**：在原有志愿者基础上发掘偏中年志愿者，今年开展"小手拉大手"活动，从儿童青少年入手拉动家长加入；本周四准备开展送春联活动，邀请书法老师写对联、由孩子上门送给老人；去年中秋节开展做月饼活动，还做过百家宴，让老人感受社区是大家庭。
-- **活动组织模式转变**：此前每次活动都由社区策划开展，2023年目标是家长自己组织、社区作为协助者。
-- **养老服务中心**：每个社区都要成立养老服务中心，提供理疗类活动，另有按摩、老年大学、心理咨询等服务。
-- **社工分类与配置**：城市社工分社区社工和街道社工两类，社区社工由小区出资专服一个小区，街道社工由政府出资负责一条街道所有小区；每个街道和乡镇派两名社工驻点，主要围绕老人和小孩服务，但很难长期坚持。
-- **社工行业困境**：社工工资低、影响就业率，很多同学做不超过一年就转行；社工服务领域分散（这次做留守儿童、下次做留守老人），专注力不集中，且服务需要花钱购买，项目资金拨不下来就结束，一年服务成效不明显——据此判断，供给不足与资金不稳定是社工制度的核心瓶颈。
-- **社工专业度欠缺**：很多社工并非社工专业出身，专业上很欠缺，可能只是图周末玩玩。
-- **心理问题老人个案**：一位老人因与邻里关系不和谐、半夜摔门等，社区派志愿者上门，但老人出现抗拒心理，觉得周围人陌生、没有关心他的人，不接受任何建议；经社工日复一日关心照料，老人与邻里关系好转、能接受意见，还主动打电话说寂寞空虚、得不到关注——据此判断，对心理封闭的老人，单纯上门探访不够，需要持续专业介入。
+## 农村养老困境与政策缺口
+- **数据事实**：据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边，仅有26.8%的老人与子女同住；发言人2引述公安数据称2021年73万多老人中约17.8%可能独居，且因1962–1965年出生人口集中退休，预计老龄化程度会进一步加剧——由此可判断独居老人基数庞大且呈上升趋势，养老服务的需求将持续扩大。
+- **案例事实**：黑龙江绥滨一位独居老奶奶因独自在家太寂寞而报警称有人敲门，民警上门后老人承认只是想找人聊天；上海一名67岁独居老人去世多日后因家中溢出刺鼻气味才被邻居发现；杭州某小区一名67岁独居老人同样在去世数天后才被发现——这些案例直接支持独居老人存在无人照料、孤独无助及意外发生后无人知晓的高风险。
+- **老人自述**：受访老人反映子女外出打工后无人陪伴，日常无人照看，连敲门无人应答的情况也无人察觉；有老人提到村里60多岁老人很多，年轻人大多外出务工——印证留守老人日常照护与情感陪伴的双重缺失。
+- **政策事实**：五保户分散供养每月生活费475元，另有护理补贴；低保标准分160、270、380元三档，按家庭状况制定；农村60岁以上老人养老金每月118元，与工人养老金待遇不同——由此可判断现行农村养老保障水平偏低，仅能维持基本生活，难以覆盖医疗、照护等额外支出。
+- **设施事实**：发言人2提到此前探索过在农村建设养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续没有支持——说明一次性建设投入后缺乏持续运营资金，设施难以长期发挥作用。
 ## 受访者提出的建议
-- **专业陪伴**：请专业社工人员进行陪伴。
-- **子女联系**：倡导在外务工子女多与老人联系。
-- **丰富文化生活**：增加更多娱乐方式，丰富老人文化生活。
-- **老年协会与固定场地**：希望老年协会专项执行、专门建养老设施，有固定场地，定期开展板报宣传、健康知识讲座等，且要考虑建设之外持续运营的经费，才能更好发挥作用。</t>
+- **发言人2建议**：请专业施工人员进行陪伴；倡导在外务工子女多与老人联系；丰富老人文化生活、增加娱乐方式；希望老年协会专项执行、专门建设养老设施，有固定场地，定期开展板报宣传或健康知识讲座，且不仅要考虑建设还要考虑后续持续运营经费，才能更好发挥作用。
+- **发言人4做法**：靠村支两委和志愿者上门串门、宣传政策、搞卫生，每月开一次党员组织会后下午开展活动，到孤寡老人、留守老人家中走访——表明基层已在现有资源下尽力开展探访，但覆盖面有限。
+## 城市社区模式与社工困境
+- **志愿者机制**：社区建立志愿者制度，一对一帮扶，志愿者发现老人住在楼下便天天上门查看，老人身体不好时帮忙送菜；定期表彰志愿者，年底可在雷锋超市用积分兑换礼品——该机制以就近帮扶降低探访成本，并通过激励维持志愿者积极性。
+- **代际带动**：今年开展"小手拉大手"活动，从儿童青少年入手拉动家长加入志愿者队伍；本周四准备开展送春联活动，邀请书法老师写对联，由孩子上门送给老人；去年中秋节开展做月饼活动，还做过百家宴——通过活动营造社区大家庭氛围，带动更多家庭参与。
+- **2023年目标**：社区目标是让家长自己组织活动，社区作为协助者——从社区主导转向居民自主运营，以减轻社区策划负担并增强可持续性。
+- **养老服务中心**：每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务——城市社区已具备较完整的养老服务设施。
+- **社工分类与困境**：社区社工由小区出资专门服务一个小区，街道社工由政府出资负责一条街道所有小区；每个街道和乡镇派两名社工驻点，主要服务老人和小孩——但社工工资低，影响就业率，很多同学做不超过一年就转行，专业社工人才流失严重。
+- **项目制局限**：社工服务按项目购买，今年做留守儿童、明年可能做留守老人，专注力分散；项目资金拨不下来就结束，但一年服务成效不一定达到——项目制导致服务不连续，难以积累长期成效。
+- **专业欠缺**：很多社工并非社工专业出身，专业能力欠缺——影响服务质量与行业长期发展。
+- **心理个案**：社工姐姐曾帮助一位心理问题老人，老人与邻里关系不和谐、半夜摔门，志愿者上门时老人抗拒，觉得周围人陌生、没有关心自己的人；经日复一日关心照料，老人与邻里关系好转，能接受意见，还主动打电话说寂寞空虚、得不到关注——说明独居老人心理问题需要长期持续介入，单纯上门探访难以解决深层心理需求。</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>42.4</v>
+        <v>45.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5309/3956</t>
+          <t>5309/3910</t>
         </is>
       </c>
     </row>
@@ -7906,111 +7917,106 @@
       <c r="C22" t="inlineStr">
         <is>
           <t># 沟通概况
-班主任林瑞在372班家长会上，面向全体家长介绍了班级基本情况、教师团队、学生存在问题及解决思路，并围绕手机管理、安全教育、家校配合等提出具体要求。班级共60人，男生25人、女生35人；教师团队多为有3年以上经验的老教师和优秀教师，班主任林瑞任教地理学科。会议还说明了保险购买、电子学生证办理、资助政策等事项，并提议成立家长委员会；家长代表张宇波（372班语文老师）分享了家庭教育经验，强调关注孩子身心健康、尊重孩子、多倾听交流。会议基调为加强家校协同，共同促进学生成长。
+班主任林瑞在372班家长会上，面向全体家长介绍了班级基本情况、教师团队、班级存在问题及解决思路、后续计划与措施，并给出家庭教育建议。班级共60人，男生25人、女生35人；教师团队多为老教师和优秀教师，班主任林瑞任教地理学科。会议还包含家长代表张宇波分享家庭教育经验、成立家长委员会（至少三人，自愿报名，已有家长自愿参加），以及保险购买、电子学生证办理、资助政策说明等事项。整体基调为加强家校协同，共同促进学生成长。
 # 沟通内容
 ## 学习表现
-- **亮点**：班级整体时间观念与执行力较强，班风班貌纪律良好，教室地面干净、卫生状况好。
-- **亮点**：学生遇到问题会积极向老师请教，班主任林瑞提到上课时会主动给学生提问机会，学生能主动上来问。
-- **亮点**：班级学生普遍关注老师反馈，会主动向老师汇报情况。
-- **需关注**：个别学生书写较差，班主任已与家长沟通，建议家长给孩子买字帖练字；班主任展示学生作业时发现班号写错（把372班写成172班）的情况。
-- **需关注**：少数学生思考能力较差，尤其在自习课上表现明显。
-- **需关注**：下次月考安排在11月初，学生已在学生手册中记录月考目标，家长可查看孩子的目标设定情况。
+- **亮点**：班级整体时间观念和执行能力较强，班风班貌纪律良好，教室地面干净、卫生状况好。
+- **亮点**：学生遇到问题会积极向老师请教，班主任林瑞表示学生上课时会主动提问。
+- **亮点**：学生关注老师、会主动向老师汇报情况，尊师意识较好。
+- **需关注**：少数学生思考能力较差，尤其在自习课上，老师在场时表现安静，老师不在时纪律混乱。
+- **需关注**：个别学生书写较差，班主任已与相关家长沟通，建议家长为孩子购买字帖练习书写。
+- **需关注**：自习课效率较低，班主任计划加强班委培训，并给予学生10分钟讨论时间，允许不懂的学生离开座位向老师请教。
 ## 行为表现
-- **亮点**：班级纪律整体良好，班风班貌得到班主任肯定。
-- **需关注**：少数同学周末沉迷玩手机游戏，玩累后上课表现懒散，约有两三个学生存在此类情况。
-- **需关注**：自习课纪律问题突出——班主任在场时学生表现安静，班主任不在时教室乱哄哄，需加强班委培训和管理。
-- **需关注**：发现少数男生有网瘾，曾发现学生在周六晚上往游戏充值（有充400元的情况），班主任提醒家长管理好手机并检查学生手机内容。
-- **需关注**：有学生观看不健康直播内容，班主任在检查中发现班级男生观看涉及暴力、不健康内容的直播。
-- **需关注**：发现学生携带镜子等物品，约10人左右，班主任要求全部收掉。
-- **需关注**：存在学生早恋现象，班主任建议家长关注孩子的QQ、抖音、快手等社交账号，注意是否被孩子屏蔽。
+- **亮点**：班级整体班风纪律良好，卫生状况佳。
+- **需关注**：少数学生周末沉迷玩手机游戏，导致返校后精神疲惫、懒散，约有两三个学生存在手机依赖问题。
+- **需关注**：发现少数男生有网瘾，有学生周末向游戏充值，金额达400元。
+- **需关注**：有学生在周六晚上外出过生日，喝酒后回校一身酒气，还抽烟、玩手机。
+- **需关注**：存在早恋现象，班主任建议家长关注孩子的QQ、抖音、快手等社交账号，留意是否有异常动态。
+- **需关注**：有学生带镜子到校，约10人左右，班主任已要求全部收掉。
+- **需关注**：有学生抽屉里发现小说，班主任建议家长管控孩子阅读内容。
 ## 社交与心理表现
-- **需关注**：学生处于初中阶段生理心理持续变化的不稳定时期，需要家长和老师共同引导。
+- **需关注**：学生处于初中阶段，生理和心理持续变化，是人生中不稳定的时期，需要家长和老师共同引导。
 - **需关注**：班主任提醒家长关注学生心理健康，发现异常应及时进行心理辅导。
-- **需关注**：有学生周末外出过生日时喝酒、抽烟，违反住校纪律要求，班主任提醒住校生周六也须遵守纪律。
-- **需关注**：班主任在班级调查中发现，知道父母生日的学生很少，建议家长加强感恩教育，引导学生体谅父母。
-## 手机管理专项
-- **需关注**：班主任要求手机统一上交，专门设置手机存放箱，每个学生名字贴好，每人对应存放。
-- **需关注**：有学生交一个手机、私留另一个，班主任提醒家长检查家中是否有多个手机，多余的要处理掉，不要留多部手机给孩子。
-- **需关注**：班主任建议家长在周一到周五不定时打电话检查，如果电话能打通但没人接，说明学生可能未交手机；如果打过去关机或停机，说明手机已上交。
-- **需关注**：班主任提醒家长关注学生手机中的社交应用（QQ空间、朋友圈、抖音、快手等），注意学生是否发布不当内容或存在早恋迹象。
+- **需关注**：班主任在班级调查中发现，只有少数学生知道父母的生日，反映出部分学生对家庭关怀意识不足，班主任已就此进行感恩教育。
 # 家长反馈
-- **家长代表身份**：家长代表为372班语文老师，同时也是学生家长，在发言中感谢学校及班主任老师的信任与付出。
-- **家庭教育理念**：强调家庭教育要关注孩子身体健康和心理健康，高中阶段仍是孩子长身体的关键时期，家长要给予营养支持，让孩子健康成长。
-- **做人教育**：认为做人是必修技能，要让孩子学会做人，不能沾染不良风气，经常对孩子说“先做人”。
-- **平常心对待**：孩子面临学习压力很大，家长要有平常心，帮助孩子正确面对挫折和失败，重新定位自己，放下眼前，向往更远的风景。
-- **尊重孩子**：孩子从小得到大人尊重，长大后也会尊重别人；要给孩子自由空间，不轻易下消极评价，不以夸耀孩子为自豪。
-- **多倾听多交流**：要多与孩子沟通，了解他们的烦恼和事件，给予更多关爱与理解。
-- **鼓励而非批评**：分享与儿子的对话，儿子问“妈妈你怎么批评我有钱”，家长回应“无论怎样，那你都是爸爸妈妈心里最优秀的儿子”，认为先批评不当，这样孩子印象更深刻。
-- **配合学校**：要遵守学校制度，配合老师工作，做一个有质量的家长。
-&gt; “无论怎样，那你都是爸爸妈妈心里最优秀的儿子”
-&gt; “先做人”
-&gt; “要给孩子一个自由空间，不要轻易给孩子下消极的评价”
-- **关注孩子身心健康**：家长代表提出要控制孩子的身体健康和心理健康，高中阶段仍是长身体关键时期。
-- **尊重孩子个性**：每个孩子都有自己的个性特点，没有适合所有人的教育方法，家长要尊重孩子的个性差异。
-- **多倾听多交流**：建议家长多倾听、多交流，了解孩子的烦恼和真实想法，给予更多关爱与理解。
-- **配合学校工作**：要遵守学校制度，配合老师工作，家校协同促进孩子成长。
+- **家长代表分享**：张宇波（家长代表）分享家庭教育经验，强调关注孩子身体健康和心理健康，教育孩子先做人、避免不良风气，家长要有平常心、尊重孩子、多倾听多交流，并配合学校制度与老师合作。
+- **家委会成立**：班主任提议成立家长委员会，至少需要三人，自愿报名，已有家长自愿参加。
+- **保险购买**：班主任建议家长为孩子购买保险，约310多元，可自行购买，最后会统计购买情况。
+- **电子学生证**：班主任说明电子学生证套餐78元（移动套餐），方便联系，能办的就办。
+- **资助政策**：班主任说明高中补助打在医保卡上、初中打在卡上，提醒家长注意补助使用，避免学生乱花。
+- **费用管理**：班主任强调不在微信群收取任何费用，由学生交给生活委员，提醒家长防范诈骗。
+- **手机管理**：班主任要求家长配合管理手机，统一上交存放，家长可不定时打电话检查，并提醒家长处理多余手机。
+- **安全教育**：班主任提醒家长关注交通安全（未满16周岁骑电动车危险）、防诈骗、防溺水、防校园欺凌。
+- **心理健康**：班主任建议家长关注学生心理健康，发现异常及时进行心理辅导。
+- **家庭教育建议**：班主任建议家长避免过分关注、放任不管、期望过高等误区，创造和睦家庭气氛，多鼓励少批评。
 # 共识与配合事项
 ## 费用与收费
-- [ ] **家长**：确认水费险收费标准（每两周2元/人），如饮用水不够再另行沟通
-- [ ] **家长**：确认书费预交11000元尚未结算，待后续结算通知
+- [ ] **家长**：确认水费险收费标准为每两周2元/人，若实际用水超出预算再另行说明
+- [ ] **家长**：确认书费预交11000元尚未结算，待最终核算后多退少补
 - [ ] **家长**：未购买书箱的同学，班主任将退还相应费用
-- [ ] **家长**：少数同学相关费用约100元左右，无无效费用约70元，具体明细班主任会另行通知
-- [ ] **家长**：班主任不会在微信群收取任何费用，需交费用由学生交给生活委员，不在微信转账
-- [ ] **家长**：警惕冒充班主任头像在群内收费的诈骗行为，不轻信群内收费消息
-## 保险事项
-- [ ] **家长**：确认学生保险费用约310元，自愿购买
-- [ ] **家长**：可选择在校购买、自行购买或通过手机平台（如阿里巴巴）购买
-- [ ] **家长**：购买后配合班主任统计购买情况
-- [ ] **班主任**：统计班级学生保险购买情况
+- [ ] **家长**：少数同学存在约100元左右的无效费用（约70元），班主任后续会逐项公布明细
+- [ ] **家长**：班主任不会在微信群内收取任何费用，所有费用由学生直接交给生活委员，请勿相信群内转账要求
+- [ ] **家长**：注意防范冒充班主任头像进行收费的诈骗行为，涉及转账务必电话核实
+## 保险
+- [ ] **家长**：建议为学生购买保险，费用约310多元，可自行选择购买渠道（学校、保险公司、线上平台均可）
+- [ ] **家长**：购买后配合班主任统计是否已购买，确保每名学生都有保障
 ## 电子学生证
-- [ ] **家长**：自愿办理电子学生证，套餐78元（移动套餐），方便联系学生
-- [ ] **家长**：班级目前有老年机且部分停机，能办理的尽量办理
-- [ ] **班主任**：将新号码发到家长群，家长需重新补充登记
-- [ ] **家长**：原坐席号码9月20几号到期，过期后无法使用
+- [ ] **家长**：电子学生证套餐为78元/月（移动套餐），方便学生请假时联系家长
+- [ ] **家长**：目前班级仅有两个可用坐席，第三个坐席将于9月20几号到期，到期后需办理新号码
+- [ ] **班主任**：将把新号码发到家长群，请家长重新登记补充
+- [ ] **家长**：能办理电子学生证的尽量办理，方便家校联系；无法办理的请说明情况
 ## 资助政策
-- [ ] **家长**：查看家长群内发布的资助政策文件
-- [ ] **家长**：高中资助与初中不同，所有补助打在学生医保卡上，需关注到账情况
-- [ ] **家长**：每次打款后与孩子确认钱款用途（生活费或带回），防止用于不当消费
+- [ ] **家长**：关注家长群内发布的资助政策文件，高中阶段所有补助将打在学生医保卡上（与初中打在卡上不同）
+- [ ] **家长**：每次补助到账后与孩子确认金额及用途，防止学生将补助用于购买手机、过生日、喝酒等非学习消费
+- [ ] **家长**：需要申请补助的学生，学校会协助办理相关手续
 ## 手机管理
-- [ ] **家长**：配合学校手机管理制度，学生手机统一上交存放箱，每人名字贴好
-- [ ] **家长**：家中多余的手机处理掉，不留多部手机，防止学生藏匿
-- [ ] **家长**：周一到周五不定时打电话检查学生手机是否上交（能打通说明未交）
-- [ ] **家长**：关注学生手机使用情况，防止网瘾、观看不健康直播等行为
-- [ ] **家长**：关注学生QQ、抖音、快手等社交账号，了解是否有早恋迹象
-## 住校纪律与安全
-- [ ] **家长**：提醒住校学生周六住校也须遵守寝室纪律要求
-- [ ] **家长**：提醒学生注意交通安全，未满16周岁不得骑电动车，尤其不得载人
+- [ ] **家长**：配合学校手机管理制度，学生手机统一上交存放，每个手机箱贴好学生姓名
+- [ ] **家长**：家中多余的手机（如家长名下办理的副卡手机）请处理掉或收回，避免学生藏匿使用
+- [ ] **家长**：周一到周五不定时拨打学生电话，若电话能打通但无人接听，说明学生可能未按时上交手机
+- [ ] **家长**：检查学生手机内容，关注是否存在网瘾、观看不健康内容、早恋等情况
+- [ ] **家长**：关注学生QQ、抖音、快手等社交账号，留意是否被屏蔽、是否有多个账号、是否发布不当内容
+- [ ] **家长**：发现学生有网瘾倾向及时干预，避免沉迷游戏
+## 住校纪律
+- [ ] **家长**：提醒住校学生遵守宿舍纪律，周六住校同样须遵守作息要求（2:10回寝室休息）
+- [ ] **家长**：提醒学生不得在宿舍内吸烟、喝酒，外出过生日须提前报备
+## 安全事项
+- [ ] **家长**：提醒学生注意交通安全，未满16周岁不得骑电动车，尤其禁止载人（载2-3人非常危险）；如确需骑行须单人骑行
 - [ ] **家长**：提醒学生注意运动安全、饮食安全
-- [ ] **家长**：提醒学生防诈骗、防溺水，不私下和陌生人外出
+- [ ] **家长**：提醒学生防范诈骗、防溺水，不得私自下河游泳
 - [ ] **家长**：关注防校园欺凌，学生遇到问题第一时间联系班主任处理
-- [ ] **班主任**：学生生活小事再小也要管好教育好，及时处理学生矛盾
+- [ ] **班主任**：学生遇到矛盾或欺凌事件，第一时间介入处理（举例：曾有一名学生11点反映矛盾，班主任12点即约谈至凌晨2点）
 ## 学习与行为管理
-- [ ] **家长**：查看学生手册，关注书写情况，个别书写差的学生需购买字帖练字
-- [ ] **班主任**：加强班委培训，提升自习课管理效率
-- [ ] **班主任**：制定详细班规，严格扣分、检讨、罚站等管理措施
-- [ ] **班主任**：严格请假制度，稳定学习秩序
-- [ ] **班主任**：定期与科任老师沟通，了解学生课堂表现
-- [ ] **家长**：关注学生月考目标（下次月考在11月初），查看学生手册中的目标设定
-- [ ] **家长**：收掉学生携带的镜子等违禁物品
-## 家校配合
-- [ ] **家长**：自愿报名参加家长委员会（至少三人，已有家长自愿报名）
-- [ ] **班主任**：组织家委会事项探讨，经班主任和家长探讨通过后成立
-- [ ] **家长**：避免教育误区——不过分关注孩子、不放任不管、不期望过高、不给过多零花钱
-- [ ] **家长**：多与孩子沟通，多鼓励少批评，适当给压力，关注心理健康
-- [ ] **家长**：创造和睦祥和的家庭氛围，不在孩子面前长时间玩手机
-- [ ] **家长**：给孩子制定容易达到的小目标，激发潜能
-- [ ] **家长**：提醒孩子合理安排饮食，注意补充营养
-- [ ] **家长**：关注孩子生活费使用情况，建议每周生活费不超过150元（早餐3-4元、午餐8元、晚餐8元）
-- [ ] **班主任**：每天进行思想教育工作
-- [ ] **班主任**：及时与家长沟通学生问题</t>
+- [ ] **家长**：查看学生手册，书写较差的学生请购买字帖练习（文具店有售）
+- [ ] **班主任**：加强班委培训，提升自习课管理效率；自习课给予学生10分钟讨论时间，不懂的问题可离开座位请教
+- [ ] **班主任**：继续每天加强思想教育工作
+- [ ] **班主任**：制定详细班规，严格请假制度，该扣分扣分、该写检讨写检讨、该罚站罚站
+- [ ] **班主任**：定期与家长沟通学生表现，及时反馈问题
+- [ ] **家长**：关注学生心理健康，发现异常及时进行心理辅导
+- [ ] **家长**：提醒学生合理安排饮食、注意补充营养
+- [ ] **家长**：鼓励学生不懂就问，主动向老师请教问题
+- [ ] **家长**：正确看待成绩，不与其他人盲目比较，帮助学生分析进步与下滑原因
+- [ ] **家长**：避免教育误区——不过分关注、不放任不管、不期望过高、不给过多零花钱
+- [ ] **家长**：控制生活费额度，建议每周不超过150元（早餐3-4元、午餐8元、晚餐8元，约21-24元/天）
+- [ ] **家长**：多鼓励少批评，给孩子制定容易达到的小目标，激发潜能
+- [ ] **家长**：创造和睦、祥和、稳定的家庭气氛，不在孩子面前长时间玩手机
+- [ ] **家长**：不在家里聚众打麻将、点外卖，给孩子安静学习环境
+- [ ] **家长**：多抽时间了解孩子在校表现，关注孩子心理动态
+## 家委会
+- [ ] **家长**：家委会至少需要3人，自愿报名，已有家长自愿参加
+- [ ] **班主任**：家委会成立后，重要事项经班主任与家长共同探讨决定
+## 其他
+- [ ] **家长**：记住班级号372班、班主任姓名（林瑞），便于家校沟通
+- [ ] **家长**：各科老师电话将发到家长群，有需要可自行联系
+- [ ] **家长**：下午3:20-3:25可前往办理相关业务（保险、电子学生证等），有一节课时间
+- [ ] **家长**：培训期间不得拍照发朋友圈或社交媒体（教官着装不允许拍照），请理解配合</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>58.8</v>
+        <v>61.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17334/3947</t>
+          <t>17334/3840</t>
         </is>
       </c>
     </row>
@@ -8091,42 +8097,39 @@
       <c r="C23" t="inlineStr">
         <is>
           <t># 例会概况
-本次周会于10月28日召开，会议等级为自愿级，由主持人召集，参会成员以团队角色为主，未提及具体姓名。会议主题为总结工作，资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。主线议题包括：工作方向与任务安排（已讨论，方向可能偏了、需考虑工作量，任务分配待定）；社区建设与成员要求（已讨论，强调社区环境、防止坏人进入，按角色划分并明确待遇与休假）；学习介绍修改（已定，将“我们是谁”提到最上面，镜头衔接调整待定）；下周工作安排（已定，邀请同事加入、完成两个活动、组建教育团队，营销工作先发介绍）。整体态势：学习介绍文件已修改完成，修订303相关文件基本完成，进展较顺；但工作方向是否偏了、任务分配具体安排、镜头衔接调整及营销工作安排等多项事项尚未明确。结论与下一步方向：下月主要任务为组建执法队伍，需招聘20多位师傅；本次以同步为主，多项待确认事项留待后续讨论。
+10月28日召开自愿级周会，主题为总结工作，会议资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。会上围绕工作方向与任务安排、社区介绍修改、任务分配与执行、待遇与休假等议题展开讨论：工作方向可能偏了、任务工作量需考虑等问题尚待定；社区介绍修改已明确将“我们是谁”提到最前面；任务分配中修订303等已接近完成，下周安排去洛阳；待遇与休假方案已同步。整体态势上，部分任务推进顺利，但工作方向与工作量问题构成当前主要卡点。会议结论为：修改学习介绍、下周安排去洛阳，下一步将邀请同事加入共同制作解决方案。目前有四个任务，包括课程开发、组建执法队伍等，下月主要任务是组建执法队伍，任务具体需招聘20多位师傅。
 # 工作进展
 ## 工作进展
-### 学习介绍与社区宣传
-- **学习介绍文件修改** ✅已完成：已将「我们是谁」提到最上面，并调整两个镜头的衔接；下一步根据会上讨论继续优化参数与细节。
-- **公众号与抖音任务** 🔄进行中：提及公众号运营与抖音任务（可视化学习方案和工具），具体执行方案待进一步明确。
-- **营销工作** 🔄进行中：计划先发介绍，后续再推进具体营销安排。
-### 任务分配与队伍建设
-- **组建执法队伍** 🔄进行中：下月主要任务，需招聘**20多位师傅**，组建教育班队；任务一第一步为确定路线、修订纲领章程。
-- **修订303相关文件** ✅已完成：已修订完毕，基本完成，待成员自行查看并确认。
-- **课程开发** 🔄进行中：当前四个任务之一，具体开发进度与分工待明确。
-- **任务分配** 🔄进行中：需考虑工作量，任务分配的具体安排尚未明确，待后续确定。
-### 社区建设与成员管理
-- **社区环境建设** 🔄进行中：强调社区环境重要，要防止坏人进入；按角色分为学生、教师、家长、学校、教育主管。
-- **待遇与休假**：上班**5000元**，额外有奖励和提成；休假为周五半天加周末两天。
-### 下周工作安排
-- **邀请同事加入** 🔄进行中：会后看有谁愿意加入，邀请其一起制作解决方案。
-- **完成两个活动** 🔄进行中：活动不是特别重要，但需大家配合完成。
-- **组建教育团队** 🔄进行中：需要确定路线，修订纲领章程，并组建教育团队。
+- **会议性质与目标**：10月28日召开自愿级周会，主题为总结工作；会议资料包括工作报告、这班看法、这班型社区介绍；目标是初步统一成员意见，统一对社区的认识。
+- **工作方向评估**：提出工作方向可能偏了，需要考虑工作量；需组建教育团队，确定路线并修订纲领章程。
+- **课程开发任务**：目前有四个任务之一，需招聘20多位师傅组建教育班队；第一步确定路线、修订纲领章程，任务开始后安排人员运行。
+- **组建执法队伍**：下月主要任务，为当前最重要任务；需具备政府资源，社区环境建设同步推进。
+- **修订303任务**：已修订了一下，应该已接近完成；需自行查看一遍后打勾确认。
+- **学习介绍修改**：已将“我们是谁”提到最上面；讨论封面和镜头衔接问题，根据修改参数调整。
+- **任务分配**：四个任务直接讲进，需说明为什么做这几件事；任务占比最大的是招聘20多位师傅。
+- **待遇与休假**：上班5000元，额外有奖励和提成；休假为周五半天加周末两天。
+- **下周安排**：安排去洛阳，需排在第二项；下一步邀请同事加入，共同制作解决方案。
+- **账单与发放**：有两个账单未发送，全场活动的优美和棒棒糖待遇尚未发放；发放完才能入职，薪资待遇月会上再发。
+- **仪表盘趋势**：今日余额比上次多，因两个账单未发送导致统计差异。
+- **会议纲要**：讨论是否还需修改，需统一思想讨论。
+- **抖音任务**：需可视化学习方案和工具，根据数据配热情况调整；每月需充值赞助。
+- **企业合规计划**：根据企业实际情况制定企业合规计划。
+- **平台维护**：讨论怎样维护好平台，有线上空间、微信、网站等渠道。
 # 协作需求
-- **邀请同事加入**：发言人1提出下周邀请同事加入，目的是让他们一起制作解决方案，需配合方为全体成员，时间节点为下周。
-- **组建教育团队**：发言人1提出需要组建一个教育团队，需配合方为全体成员，时间节点未明确。
-- **完成两个活动**：发言人1提出下周要完成两个活动，虽说明活动不是特别重要，但需要大家互相理解并配合完成，时间节点为下周。
-- **营销工作先发介绍**：发言人1提出先把营销工作发介绍，需配合方为全体成员，时间节点未明确。
-- **任务分配调整**：发言人1指出任务分配需考虑工作量，并提及「张经理」需要修改任务安排，将「下周去洛阳」的事项排到第二项，需配合方为张经理，时间节点为下次会议前。
-- **学习介绍镜头衔接调整**：发言人1提出学习介绍中两个镜头的衔接需要调整，需配合方为负责修改文件的人员，时间节点未明确。
-- **会议纲要修改**：发言人1询问「这个会议纲要还要改吗」，并提出要加新的任务，需配合方为全体成员，时间节点未明确。
-- **线下继续学习**：发言人1提出会议时间已长，建议在线下继续一起学习，需配合方为全体成员，时间节点为会后。</t>
+- **邀请同事加入**：发言人1提出下一步邀请同事加入，共同制作解决方案，会后将看有谁愿意参与；需相关成员配合确认参与意向。
+- **学习介绍修改**：发言人1已完成学习介绍修改（将“我们是谁”提到最上面），下一步需相关成员配合审阅并确认封面与镜头衔接的修改效果。
+- **任务分配与执行**：发言人1提出任务分配需安排，涉及修订303等任务已接近完成，需相关成员配合查看并确认修订结果。
+- **下周去洛阳安排**：发言人1安排下周去洛阳，需相关成员配合确认行程及任务优先级排序。
+- **会议纲要修改**：发言人1询问会议纲要是否还需修改，需相关成员配合反馈意见。
+- **待遇与休假确认**：发言人1提及待遇为上班5000元、额外奖励和提成，休假为周五半天加周末两天，需相关成员配合确认执行细节。</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>30.6</v>
+        <v>26.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4999/1554</t>
+          <t>4999/1417</t>
         </is>
       </c>
     </row>
@@ -8583,40 +8586,38 @@
       <c r="C24" t="inlineStr">
         <is>
           <t># 就诊概况
-48岁男性患者张春和，在成都轻工研究所从事科研工作，因上腹烧灼痛4年、近3个月加重，于消化内科就诊。严医生接诊，初步判断需排查消化道出血及胃部病变，建议留大便做潜血检查并预约胃镜。
+48岁男性患者张春和，在成都轻工研究所从事科研工作，于消化内科门诊就诊。主诉上腹烧灼痛4年、近3个月加重，伴两次黑便及近期反酸呕吐。医生初步判断需排查消化道出血及幽门梗阻可能，建议留大便查潜血并预约胃镜。
 # 病史与背景
-- **现病史**：上腹烧灼痛4年，每年春季多发，近3个月加重；疼痛位于心窝处，与进食冷、硬、辛辣食物及工作紧张劳累相关，与油腻食物关系不大；近3个月白天发作，无夜间痛醒，疼痛可忍受，有完全不痛的时候。
-- **黑便史**：近4年出现两次黑便，一次在一年前，一次在三个月前，每次持续约一个月，大便干、形状正常，每日最多两次；两次均住院两三天后大便转黄。
-- **伴随症状**：最近两个月出现反酸呕吐，呕吐物为酸水，含当日或隔日食物，呕吐后舒适。
-- **既往史**：16岁时患甲肝，在三医院住院一个月，出院及此后体检肝功能均正常；小学时因扁桃体炎在儿童医院就诊。
-- **过敏史**：小学时因扁桃体炎服用磺胺药后左手起红疹，持续半个月，医生诊断为药物过敏，此后禁用磺胺药。
-- **家族史**：父亲76岁有低血压，母亲75岁有冠心病（服药控制良好），弟弟身体健康，婶婶（叔叔的爱人）患胃癌。
-- **个人史**：在成都轻工研究所从事科研工作，工作紧张，经常加班熬夜；吸烟史，以前每日一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝；每日喝两杯淡茶。
-- **近期用药**：近期服用斯达舒，初有效后效果不佳，剂量从每日两次每次一颗增至每日四五次；另服用奥美拉唑（武汉产）、阿莫西林及单位医务室自配胃炎合剂，停药后症状反复。
+- **现病史**：上腹心窝处烧灼感疼痛4年，每年春季多发，近3个月加重；进食冷、硬、辛辣食物或工作紧张劳累时诱发，白天发作，无夜间痛醒，疼痛可忍受，有完全不痛的时候。
+- **黑便史**：一年前及三个月前各出现一次黑便，每次持续约一个月，均住院数日好转；近3个月大便正常，无黑便。
+- **反酸呕吐**：近2个月出现数次呕吐，呕吐物为酸水，含早晨或中午食物，有时含隔夜食物，呕吐后舒适。
+- **既往史**：16岁患甲肝，在三医院住院一个月，出院及此后体检肝功能均正常；小时候因扁桃体炎在儿童医院就诊。
+- **过敏史**：小时候因扁桃体炎服用磺胺药后左手起红疹，持续半个月，诊断为药物过敏，此后禁用磺胺药。
+- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；婶婶（叔叔的爱人）患胃癌，患者担心自己是否也会得胃癌。
+- **个人史**：吸烟，以前每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝，应酬时少量；每天喝两杯淡茶；双眼近视400度，偶尔口腔溃疡。
+- **近期用药**：近期服用斯达舒，最初一天两次每次一颗有效，后效果不佳，现加至每天四五次仍效果不好；还服用过奥美拉唑（武汉药厂产，国产）和阿莫西林，以及医务室自配的胃炎合剂，服药好转后停药则症状反复。
 # 诊断与检查结果
-未提及
+医生初步判断患者上腹烧灼痛与饮食及劳累相关，结合两次黑便史需排查消化道出血，反酸呕吐物含隔夜食物提示可能存在幽门梗阻。尚未进行胃镜及大便潜血检查，待检查后由上级张医生（指导教授）进一步判断。
 # 治疗方案与医嘱
-- **检查安排**：留大便做潜血检查，以排查出血。
-- **检查安排**：预约胃镜，因患者爱人后天可请假陪同，安排在后天进行。
-- **生活方式**：建议戒烟、尽量少喝酒，因吸烟饮酒对胃肠道疾病影响较大。
-- **生活方式**：注意避免熬夜，因工作紧张、经常熬夜可能诱发或加重症状。
-- **复诊与陪同**：胃镜检查需有家属陪同，患者爱人将请假陪同。
-| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
-| --- | --- | --- | --- | --- |
-| 斯达舒 | 未提及 | 每日四五次（原为每日两次每次一颗） | 口服 | 初有效后效果不佳，剂量已增加 |
-| 奥美拉唑 | 未提及 | 未提及 | 口服 | 武汉产，停药后症状反复 |
-| 阿莫西林 | 未提及 | 未提及 | 口服 | 未提及 |
-| 胃炎合剂 | 未提及 | 未提及 | 口服 | 单位医务室自配 |
+- **检查安排**：留大便做潜血检查，以排查出血；预约胃镜，因患者爱人后天可请假陪同，改至后天进行。
+- **生活方式**：建议戒烟、尽量少喝酒，因吸烟饮酒对胃肠道疾病有影响；注意休息，避免熬夜劳累。
+- **复诊与陪同**：胃镜后天进行，由爱人陪同；医生将向上级张医生汇报病情后，再商定下一步处理意见。
+| 药品名称 | 用法用量 | 注意事项 |
+| --- | --- | --- |
+| 斯达舒 | 最初一天两次，每次一颗；现加至每天四五次 | 效果逐渐不佳 |
+| 奥美拉唑 | — | 武汉药厂产，国产 |
+| 阿莫西林 | — | — |
+| 胃炎合剂 | — | 医务室自配 |
 # 复诊与预警信号
-未提及</t>
+胃镜预约在后天进行，由爱人陪同。⚠️ 若再次出现黑便或呕吐物带血，需立即就医。</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10297/1118</t>
+          <t>10297/1139</t>
         </is>
       </c>
     </row>
@@ -8955,105 +8956,133 @@
       <c r="C25" t="inlineStr">
         <is>
           <t># 讲座概况
-肖楠总在本次专项讨论会上向投资者汇报过去一年的研究布局、研究成果及投资框架的反思与更新。他首先阐述知识与信息的鸿沟，强调投资者应关注可研究的问题，并介绍市场上两大投资流派（巴菲特代表的务实派与索罗斯代表的务虚派），自认偏务实派。他明确反对抱团与均值回归两种流行观点，认为抱团定义不本质，基金经理间是竞争关系；均值回归是局部正确，90%时间正确但10%错误代价惨重，收益率呈幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。肖楠确定互联网、财富管理、新消费、高端制造为四大重点研究布局方向，并提出五点投资框架反思：世界上没有一劳永逸的坐地收钱生意；从熵增角度理解商业模式更本质；存在长期变量（如国运、文化背景）影响收益率；深度价值可能长期无效；企业增长存在X factor（曲率因素）。在客户问答环节，肖楠就中期投资机会、伟大公司判断标准、全市场基金选股逻辑、血制品行业、农林牧渔行业、熵增分析、增长曲线、财富管理行业、企业家精神等问题逐一回答。
+肖楠总在本次专项讨论会上向投资者汇报过去一年的研究布局、研究成果及投资框架的反思与更新。他首先阐述知识与信息的鸿沟，强调投资者应关注可研究的问题，并介绍市场上两大投资流派（巴菲特代表的务实派与索罗斯代表的务虚派），自认处于中间偏左位置。肖楠明确反对市场上流行的“抱团”和“均值回归”两种观点，认为“抱团”定义不本质，基金经理之间是竞争关系，主观上不可能抱团；均值回归是局部正确，长期看收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。过去一年研究资源投入四个方向：互联网、财富管理行业、新消费和高端制造。投资框架反思共五点：商业模式分类不完备、从商增角度理解商业模式更本质、企业家精神无法定价但长期视角下可能带来超额收益、因终局判断悲观错过中期10倍投资机会、长期变量（如国运、文化背景）可能解释相当部分收益率来源。另有两项补充反思：深度价值可能长期无效（打问号）、小企业X factor驱动企业增长且不被线性描述的因子。客户问答环节，肖楠就终局判断与中期机会、伟大公司判断标准、全市场基金选股逻辑、血制品行业、农林牧渔行业、商增分析、增长曲线、财富管理行业、企业家精神等问题进行回答。
 # 核心观点与论证
 ## 知识与信息的鸿沟
-- **核心区分**：肖楠认为投资者关心的"What happen next"类问题，得到的答案只是信息而非知识；他看好某板块是基于相关知识（knowledge），但听众得到的仅是一条"肖楠看好某某"的信息，知识与信息之间存在巨大鸿沟。
-- **观点易变**：肖楠举例称今天看好某板块，明天可能因新知识增加而修正判断，但投资者可能需要等一年甚至更长时间才知道观点已变，因此这类答案对投资者实际用处不大。
+- **核心观点**：投资者关心的"What happen next"类问题，得到的答案只是信息而非知识，知识与信息之间存在巨大鸿沟。
+- **论据**：肖楠看好某板块或个股，对他而言是基于相关知识（`knowledge`），对投资者而言得到的仅是一条"肖楠看好某某"的信息。
+- **论据**：肖楠今天的观点明天可能因新知识增加而修正，但投资者可能需要等一年甚至更长时间才知道观点已变。
 ## 问题分类框架
-- **四类划分**：肖楠基于自身研究框架，将问题分为重要不重要、可研究以及难以研究四类，他关心的是标的基本面是否变化、投资逻辑有没有更新、对标的认知是否更深入领先。
-- **框架自省**：作为基金经理，肖楠最关心自身投资框架有无值得修正和更改之处，他认为这些问题可被研究，在此"挖井打矿"是负矿。
-- **因人而异**：该表仅针对肖楠个人，例如基于宏观变量做资产配置的人，美联储利率变化对市场的影响就是既重要又可研究的问题。
+- **核心观点**：肖楠将问题分为重要不重要、可研究以及难以研究四类，只关心可研究的问题。
+- **论据**：肖楠关心标的基本面是否发生变化、投资逻辑有没有更新、对标的的认知是否更深入领先。
+- **论据**：作为基金经理，肖楠最关心自己的投资框架有无值得修正和更改的地方，这些是可被研究的。
+- **论据**：该表仅针对肖楠个人，例如基于宏观变量做资产配置的人，美联储利率变化对市场的影响就是既重要又可研究的问题。
 ## 两大投资流派
-- **极端务实派**：以巴菲特为代表，认为股票是企业所有权的一部分，价值来源是企业价值即未来现金流，短期波动是随机的、不值得研究，研究重点应放在公司生意和管理层上，买入后长期持有直到投资逻辑变化。
-- **极端务虚派**：以索罗斯为代表，认为股票是筹码，价值来源于其他交易者对筹码的看法，交易代表信息、股价波动代表信息，不仅要研究基本面，更要研究交易者基于基本面的行为，通过交易与市场对话、试错并获利。
-- **中间位置**：大部分基金经理包括肖楠都处于两个极端中间的某一位置，肖楠自认偏巴菲特一派；务实还是务虚没有高下之分，做好的都是大师，做不好都是东施效颦。
-## 反对抱团观点
-- **定义不本质**：肖楠认为"抱团"这个定义不本质，会导致研究误入歧途；他举例称若给一叫太阳就出来的动物起名"光明使者"，这个定义不本质，因为太阳出来与动物叫没有因果关系。
-- **主观无意愿**：基金经理之间是竞争关系，主观上没有任何抱团意愿，每个基金经理都想买跟别人不一样的东西并获得市场认可；不可能出现打电话给嘉实基金王经理商量一起买股票的情况。
-- **研究推荐非抱团**：同一家基金公司研究员推荐股票、多位基金经理认可后买入，若将此定义为抱团则荒谬；肖楠反问是否要"抽取三位幸运基金经理"才能买研究员推荐的股票。
-- **截面数据局限**：抱团是截面上的数据，忽略了时间维度变化；肖楠称自己8年前、5年前就买了某些标的，突然一大堆人蜂拥而至，他其实也一脸懵；A股和海外股市都有类似现象，如当年的五朵金花、眉飞色舞、长牛的医药消费等。
-## 反对均值回归
-- **局部正确**：均值回归即"跌多了要涨、涨多了要跌"，短期看K线图确实如此，但拉长看无法解释10年涨10倍、20倍、50倍、100倍的长线牛股。
-- **案例教训**：肖楠的研究员是某商学院毕业生，其老师在海螺水泥上做波段，过去10年赚了约两三倍，技术指标非常准；2016年或2017年涨了一波后卖掉等回调，结果两年时间股票涨了五六倍，再也没能买回来。
-- **幂律分布**：收益率是幂律分布而非正态分布，投资核心是找到摆脱"涨多了就跌、跌多了就涨"这种局部正确规律的长线超级大牛股；美国股市200年价值增量由4%的公司贡献，把那4%的公司挖掉，200年来美国股市没有涨。
+- **核心观点**：市场上基金经理的理念和方法大致处于巴菲特代表的极端务实派与索罗斯代表的极端务虚派两个极端之间。
+- **论据**：巴菲特一派认为股票是企业所有权的一部分，价值来源是企业价值即未来现金流，短期波动是随机的、不值得研究，应买入长期持有直到投资逻辑变化。
+- **论据**：索罗斯一派认为股票是筹码，价值来源于其他交易者对筹码的看法，交易代表信息，应研究交易者基于基本面的行为，通过交易与市场对话、试错并获利。
+- **论据**：大部分基金经理包括肖楠处于两个极端中间某一位置，肖楠自认偏巴菲特一侧。
+- **论据**：务实还是务虚没有高下之分，做好的都是大师，做不好都是东施效颦，理念没有好坏。
+## 反对"抱团"说法
+- **核心观点**：肖楠明确反对"抱团"说法，认为该定义不本质，会导致研究误入歧途。
+- **论据**：定义不本质的比喻——若给一叫太阳就出来的动物起名"光明使者"，按此思路理解会误以为宰了它太阳就不出来。
+- **论据**：基金经理之间是竞争关系，主观上不可能抱团，不存在打电话给嘉实基金王经理商量一起买股票的可能。
+- **论据**：同一家基金公司研究员推荐股票获广泛认可、大家买入，若定义为抱团则荒谬，否则需抽取三位幸运基金经理才能买，不可能。
+- **论据**：抱团是截面数据，忽略时间维度；肖楠8年前、5年前买入的标的突然被蜂拥买入，拉长时间看A股和海外股市都有此现象，如当年的五朵金花、眉飞色舞、长牛的医药消费。
+## 反对"均值回归"
+- **核心观点**：肖楠明确反对"均值回归"思想，认为它是特别不本质的局部正确。
+- **论据**：短期看K线图确实均值回归，涨多了跌、死叉金叉，但拉长看无法解释长线牛股10年涨10倍、20倍、50倍、100倍的现象。
+- **论据**：某商学院老师在海螺水泥上做波段，过去10年赚约两三倍，2016或2017年卖出后等回调，两年内股价涨了五六倍，再也没能买回来。
+- **论据**：均值回归90%的时间都正确，但10%的错误代价惨重。
+- **论据**：收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献，挖掉这4%的公司美国股市200年来没有涨。
 ## 四大研究布局
-- **互联网**：全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业——第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）；开通港股通后可投资以前在A股无法投的公司，不能容忍错失机会。
-- **财富管理**：中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，由于巨大基数效应和收入分布密度效应，会有巨额剩余财富有待专业机构管理，行业潜在空间远超想象。
-- **新消费**：从匮乏年代走出来的第一代、第二代消费品公司，与富裕年代诞生的新消费公司完全不同——从CEO想法理念、组织架构、经营理念到生产方式、营销方式都截然不同；随着中国越来越富裕，此类公司会越来越多。
-- **高端制造**：中国几乎是全球唯一拥有全产业链的国家；在非常多的制造业细分领域，中国已不是被卡脖子，而是客气地讲"占据主导地位"；与10年前"10亿双袜子换台飞机"的理解完全不同，欧美日企业手中的市场份额已是中国企业"碗里的肉"。
-## 新消费研究认知
-- **产品差异巨大**：从外人角度看两家公司产品差不多（卖笔或卖电饭锅），但收入利润体量差距巨大；深入研究发现，在产品经理团队或CEO眼中，自家产品与竞争对手产品存在巨大鸿沟，这些差异在三年、五年、十年维度会被放大得非常大。
-- **行业格局差异**：传统消费领域龙头赚钱，龙二龙三也赚钱，只是差一点；新消费领域同样巨大的行业里可能只有两家公司，一家赚很多钱，另一家完全不挣钱、不知道该怎么挣钱。
-## 商业模式反思
-- **三类划分**：肖楠将生意分为三类——坐地收钱（最喜欢买）、苦尽甘来、燃烧自己照亮别人（不值得买）；至今依然这样划分，也相信对商业模式的理解非常好。
-- **框架不完备**：世界上没有一劳永逸的坐地收钱生意，极端稀缺；哪怕爱马仕这样的企业，一个设计师的好坏也可能影响未来五年十年的销售；长期看所有企业都要死去，若单一从这个维度出发会错失很多机会。
-## 熵增视角
-- **更本质的理解**：从熵增角度理解商业模式某种程度上更本质；一些企业从诞生到收入和利润涨100倍，结构跟诞生之时没有特别大的区别，商没有怎么增加就能放大100倍；另一些企业扩张过程中熵增剧烈，熵增到一定程度后科斯定理告诉我们企业已没有存在必要。
-- **研究重点**：过去一段时间大量讨论企业在成长过程中靠什么吸收企业成长的熵增，这是第二点心得。
-## 长期变量反思
-- **国运变量**：西方世界过去对中国的判断中，没人预料到中国和平稳定高速发展30多年、40年；中国每一年都遇到困难，但最后都发现高速发展，这是一个隐藏的巨大变量，称作国运有点不对但也有一点对。
-- **茅台案例**：过去买茅台赚钱的人写的回忆录中，投资逻辑包括便宜、产品好、商业模式好等，但这些逻辑加在一起能否解释过去十年、二十年茅台如此巨大的涨幅？别的股票也有类似逻辑，为什么涨得没有茅台多？可能有一个更大的变量在起作用——中国的宏观经济背景、文化背景、茅台的品牌背景等。
-- **奢侈品牌案例**：LV、爱马仕等顶级奢侈品牌讲的故事是"祖上给皇上当过马夫、给娘娘当过皮匠"，但给的是英国、法国这些老牌资本主义国家的皇上和娘娘，因为他们的军舰当年横扫全世界；20年前天涯论坛上问中国GDP何时超过日本被群嘲，今天大家在算哪一年GDP超过美国。
-- **白酒出海逻辑**：欧美人不喝白酒，普遍答案是"不好喝"，但肖楠认为可能不是正确答案；30年前、20年前洋酒刚进入中国时，中国土豪兑雪碧喝，因为难喝才兑雪碧，难喝还要喝是因为人家的文化是强势文化；如果有一天中国国力强盛到能在人家十二海里外做军事演习，就可以讲"纯粮固态发酵的酒才是好酒，whisky、白兰地、清酒都是液态发酵法做出来的，特别不值钱"这个故事。
-- **研究启示**：要经常对市场保持谦卑，穷尽所有智慧精力探究收益率来源，往往依然忽略一个巨大的变量；未来研究会把一些特别隐性的、可能在一个十年维度上起作用的长期变量纳入研究框架。
-## 深度价值反思
-- **结果而非原因**：深度价值只是一个结果，导致深度价值的原因不变，那么深度价值最好的结果也就是不输了；去年投了一些认为是深度价值的标的，结果非常差，产生了很大启发和刺激。
-- **未定结论**：深度价值可能长期无效，肖楠打了问号，没有得到结论。
-## X factor（曲率因素）
-- **线性假设局限**：做DCF、DDM都是线性假设，无非是增长率12%、13%还是15%、16%、17%的区别；但拉长到10年视角，企业发展是一条非常漂亮的曲线，经典投资模型没有一个变量隐含对企业发展曲率的估计。
-- **X factor定义**：驱动企业增长且不被线性描述的因子，经典投资理论模型无法定价，但长期起作用的就是这些；即使无法有效定价，也一定要承认其存在，否则会陷入"企业挺好但估值贵、企业便宜但基本面烂"的困境。
-- **案例说明**：5年前、10年前大家说某些企业产品渗透率已很高、利润率已很高，但到今天看当年说的全部没有实现，这些企业长出了第二生长曲线、第三生长曲线，还在找新的生长曲线；超额认知就来自于这些方面。
-## 中期机会反思
-- **错过十倍机会**：过去错过一些特别大的机会，因判断行业终局可能不大行而放弃，最打脸的是明明判断对了，却在两三年的时间里深深错过十几倍的涨幅。
-- **复盘发现**：这些企业某一代产品当时领先，后来确确实实如预判被人追上，但企业深深做出了第二增长曲线，且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。
-- **调整策略**：在坚持对终局重要性判断的基础上，也要争取研究格局演进的阶段性特征来把握投资机会；通过紧密跟踪认知快速迭代、关注里程碑式事件，在中期时间内获得好的投资回报率。
+- **核心观点**：过去一年研究资源投入四个方向：互联网、财富管理行业、新消费和高端制造。
+- **论据**：互联网——全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业：第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）。
+- **论据**：互联网领域未来仍会出特别大的机会，港股通开通后可投资以前A股未上市的互联网公司。
+- **论据**：财富管理——中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，因巨大基数效应和收入分布密度效应会有巨额剩余财富有待专业机构管理，行业潜在空间远超想象。
+- **论据**：新消费——新一代消费公司从CEO的想法理念到基层执行人员、生产方式、营销方式，与匮乏年代出来的企业完全不一样，不是产品够新而是组织架构和经营理念完全不同。
+- **论据**：高端制造——中国是全球几乎唯一拥有全产业链的国家，微观深入很多制造业细分领域会发现中国已占据主导地位，与10年前"10亿双袜子换台飞机"的理解完全不同；欧美日企业可得的市场份额已是中国企业碗里的肉。
+## 新消费领域研究成果
+- **核心观点**：新消费领域看起来产品差不多的公司，收入利润体量差距巨大，产品差异在三年五年十年维度被放大。
+- **论据**：从外人角度看两家公司卖笔或电饭锅看起来差不多，但深入研究发现产品经理团队或CEO眼中自家产品与竞争对手产品存在巨大鸿沟。
+- **论据**：传统消费领域龙头赚钱、龙二龙三也赚钱，但新消费领域同样巨大的行业里两家公司，一家赚很多钱、另一家完全不挣钱也不知道怎么挣钱。
+- **论据**：从商增角度理解企业商业模式，成长企业商增速度差异巨大，商增过快导致企业走向失败，商增是理解商业模式的重要角度。
+## 投资框架反思一：商业模式分类不完备
+- **核心观点**：过去将生意分为坐地收钱、苦尽甘来、燃烧自己照亮别人三类，但该框架存在不完备性。
+- **论据**：世界上没有一劳永逸的坐地收钱生意，极端稀缺，哪怕爱马仕也会因一个设计师的好坏影响未来五年十年销售。
+- **论据**：长期看所有企业都要死去，不能抱着买千秋万代企业的想法，单一维度出发会错失很多机会。
+## 投资框架反思二：商增角度更本质
+- **核心观点**：从商增角度理解商业模式某种程度上更加本质。
+- **论据**：一些企业从诞生到收入和利润涨100倍，企业结构与诞生之时没有特别大区别，商没有怎么增加就轻易放大100倍。
+- **论据**：另一些企业扩张过程中商增剧烈增加，商增到一定程度后柯斯定理告诉我们企业已没有存在必要。
+- **论据**：过去大量讨论企业在成长过程中靠什么吸收熵增，这是第二点心得。
+## 投资框架反思三：企业家精神定价问题
+- **核心观点**：与张坤争论企业家精神或企业家值不值得定价，无法定价但长期视角下可能带来超额收益。
+- **论据**：企业如日中天时说企业家优秀、估值给50倍，企业犯错误时说企业家不行，导致无法给企业家定价。
+- **论据**：过去特别希望买谁做都一样的生意（如茅台，领导人抓了一批又一批不影响销售），但反过来想，没有这样的公司是否就不投了。
+- **论据**：即使无法给企业家定价，企业发展中一些要素可能在长期视角下带来超额收益，尤其在困难时期，这弥补了三种商业模式分类忽略的因素。
+## 投资框架反思四：终局判断与中期机会
+- **核心观点**：因终局判断悲观错过中期10倍投资机会，应坚持终局判断同时争取研究格局演进的阶段性特征。
+- **论据**：过去投研中因判断企业终局不太好或看不清楚，放弃了一些中期投资机会，甚至错过10倍投资机会。
+- **论据**：具体案例——某企业产品跨代领先竞争对手，当时判断领先不能长期保持、行业格局会变差、ROE剧烈下降，判断正确但企业后来涨了十几倍，过程完全错过。
+- **论据**：可通过紧密跟踪认知快速迭代、识别里程碑式事件来提高胜率，在中期时间内获得好的投资回报率。
+## 投资框架反思五：长期变量
+- **核心观点**：一些特别长期的变量解释了相当一部分收益率来源，需保持谦卑并纳入研究。
+- **论据**：为什么日本、德国、越南没有出巴菲特、索罗斯这样的投资大师，美国有；中国股市20多年诞生一批长线收益好的基金经理，放到台湾、日本、韩国不一定有同样收益率。
+- **论据**：西方世界过去对中国判断中没人预料到中国和平稳定高速发展30多年、40年，这是一个隐藏的巨大变量，称作国运有点不对但也有一点对。
+- **论据**：过去买茅台赚钱的人写的回忆录中列出的逻辑（便宜、产品好、商业模式好）加在一起无法解释茅台过去十年20年如此巨大的涨幅，可能有更大的变量（宏观经济背景、文化背景、品牌背景）在起作用。
+- **论据**：LV、爱马仕等奢侈品牌讲的故事是祖上给皇上当马夫、给娘娘当皮匠，但给的是英国、法国这些老牌资本主义国家的皇上娘娘，因为他们的军舰当年横扫全世界。
+- **论据**：20年前天涯论坛帖子问中国GDP何时超过日本被群嘲，今天大家在算哪一年GDP超过美国。
+- **论据**：30年前洋酒刚进入中国时土豪兑雪碧喝，因为难喝但文化强势、为显示高档；若中国国力强盛到航母在人家十二海里外军事演习，就能讲"纯粮固态发酵的酒才是好酒"的故事。
+- **论据**：未来研究将把特别隐性的长期变量（十年维度起作用）纳入研究。
+## 深度价值可能长期无效
+- **核心观点**：深度价值可能长期无效（打问号，未得结论）。
+- **论据**：深度价值只是一个结果，导致深度价值的原因不变，深度价值最好的结果也就是不输。
+- **论据**：过去投了一些认为是深度价值的标的，结果非常差，产生很大启发和刺激。
+## 小企业X factor
+- **核心观点**：驱动企业增长且不被线性描述的因子（X factor），经典模型无法定价但必须承认存在。
+- **论据**：做DCF、DDM都是线性假设，无非增长率是12、13、14还是15、16、17的区别，但拉长10年视角企业的发展是一条非常漂亮的曲线。
+- **论据**：某理科背景的知名创业家讲企业的发展类似于用直线逼近曲线，短期看线性增长，长期看是曲线。
+- **论据**：经典投资模型中没有变量隐含对企业发展曲率的估计，但现实中大量行业、企业做着同样的事情、生产差不多的产品，差异巨大，原因就是曲率因素在起作用。
+- **论据**：今年遇到的现象——一些企业挺好但估值贵，一些企业便宜但基本面很烂，怎么投是挣扎中的问题。
+- **论据**：今天涨得很大的企业，5年前10年前大家说产品渗透率已很高、利润率已很高，但到今天看当年说的都没实现，企业长出第二、第三生长曲线，这就是有X factor。
+- **论据**：经常强调的超额认知就来自于这些方面。
 # 金句总结
 &gt; 知识和信息之间是有着巨大的鸿沟的。
-- 讲到投资者关心的"What happen next"问题时，指出投资者得到的只是信息而非知识。
+- 讲到投资者关心的"What happen next"问题：主讲人认为听众得到的只是"肖楠看好某某"的信息，而非支撑判断的知识。
 &gt; 务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。
-- 对比巴菲特代表的务实派与索罗斯代表的务虚派时，强调投资理念没有好坏之分。
+- 对比巴菲特代表的务实派与索罗斯代表的务虚派时，强调投资理念本身无好坏，执行结果才分高下。
 &gt; 均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。
-- 反对均值回归观点时，用商学院老师在海螺水泥上做波段最终踏空的案例说明。
-&gt; 200年以来，美国股市的价值增量，是由4%的公司贡献的。
-- 论证收益率呈幂律分布而非正态分布，说明长线牛股贡献绝大部分收益率。
-&gt; 这个世界上其实没有一劳永逸的坐地收钱的生意。
-- 反思过去对三种商业模式分类的局限时提出，长期看所有企业都会死去。
-&gt; 我们尽管穷尽了我们所有的智慧，所有的精力去力求探究我们的这个收益率的来源，往往依然是忽略了一个巨大的变量在后面起作用。
-- 讨论长期变量对收益率的影响时，以日本为何没有巴菲特、茅台涨幅难以用常规逻辑解释为例。
-&gt; 深度价值它只是一个结果，是导致这种深度价值的原因不变，那么深度价值，那么它最好的得到的结果也就是不输了。
-- 反思深度价值投资方式时提出，深度价值可能长期无效，打了问号。
+- 反对均值回归观点时，以某商学院老师在海螺水泥上做波段、卖出后两年股价涨五六倍再也买不回来的案例佐证。
+&gt; 收益率是幂律分布的，不是正态分布的。
+- 论证均值回归不成立时提出，并引用美国股市200年价值增量由4%公司贡献的数据。
+&gt; 深度价值它只是一个结果，是导致这种深度价值的原因不变，那么深度价值它最好的得到的结果也就是不输了。
+- 反思深度价值投资方式为何长期不成功时提出，并承认自己投深度价值标的结果非常差。
 &gt; 驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。
-- 提出企业增长存在X factor（曲率因素），经典投资模型无法定价但长期起作用。
+- 提出小企业X factor概念时强调，经典投资模型无法定价曲率因素，但长期起作用的正是这些因素。
+&gt; 我们一定要把底线的风险搞好。我们一致同意的就是这个东西它不可被定价。
+- 回答如何把握企业家精神时强调，避免因对企业家认可而犯投资错误，企业家精神不可定价、须谨慎使用。
+&gt; 我们有一些深度的、长期的变量可能是我们所忽略的。
+- 反思长期变量对收益率来源的解释力时提出，并以中国GDP超过日本、白酒出海等话题说明国运等隐性变量的作用。
 # Q&amp;A 环节
-**听众**：您刚刚讲到在重视终局结果的过程中，也更加关注格局演进中的阶段性特征和中期投资机会，能否再详细描述一下？
-**肖楠**：这个想法最早来自我们过去错过的一些特别大的机会。我们当时判断某些行业终局可能不大行，而最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，这类企业有一个重要特征是我们当时忽略的——比如某代产品当时领先，后来确实如我们所料被人追上，但企业又做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。所以后来我们在一些投资里，开始承认终局可能没有那么强、不会像一劳永逸躺着收钱那么强，但在这个前提下依然做出好的投资来。具体标的不太好说，确实有一两个标的给我们带来极大的刺激。
-**听众**：您在年报中讲到坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有具体的财务指标？
-**肖楠**：伟大公司是在财务指标里面看不出来的。个股没办法在公开场合说，我举一个例子：A、B两家企业同属一个大行业但不同细分子行业，投资逻辑很像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高。区别在于，B公司不怎么做研发，靠管理上精益求精，业内络绎不绝来学习但学不会；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人和日本人手里。有意思的是这两家都是国企，A公司在发展初期被德国人、日本人狠狠坑过，从董事长到技术骨干积攒了非常强烈的产业报国、技术报国的情绪，从跟着学、越做越强、超越对手、对手跑过来学，到开始做全产业链布局，写下来就是一个产业史诗。这种企业堪称伟大。
-**听众**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对消费以外行业的选股主要基于什么逻辑？
-**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，就是以前讲过的不可能三角、企业三阶段、三种商业模式这些。只不过消费行业基金只许买消费，所以只能在消费行业里选，两者的选股逻辑完全一样，没有什么区别。
-**听众**：您怎么看待血制品行业的竞争壁垒？
-**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒，这个就不展开了。我们找了一堆强壁垒的公司，相比之下买了另外一些。
-**听众**：在管理行业能否再具体讲一下？
-**肖楠**：血制品这个行业我们研究得不是特别多，因为我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有特别冲突的观点。
-**听众**：农林牧渔行业有所提升，请问您对这个行业的观点？
+**主持人**：有客户提问，您刚刚讲到在重视终局结果的同时，也更加关注格局演进过程中的阶段性特征和中期投资机会，能否再详细描述一下？
+**肖楠**：这个想法最早来自我们过去错过的一些特别大的机会。我们当时判断某些行业的终局可能不大行，而最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，这类企业有一个重要特征是我们当时忽略的：比如某一代产品当时领先，后来确确实实如我们所料被人追上，但这个企业却做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。所以我们在后来的投资里，开始接受终局可能没有那么强、不会像一劳永逸躺着收钱那么强的判断，在这个前提下依然做出好的投资，希望未来不要再错过类似机会。具体标的我不太好说，但确实有一两个标的给我们带来极大的刺激。
+**主持人**：您在年报中也讲到坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有一些具体的财务指标？
+**肖楠**：伟大公司是在财务指标里面看不出来的。我举一个例子，不能说具体企业：A、B两家公司同属一个大行业但不同细分子行业，投资逻辑很像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高，精细化管理能力和对产品的理解都非常好。但A公司和B公司有一点不一样——B公司不怎么研发，靠管理精益求精做到成本极低，壁垒在于业内络绎不绝来学习但学不会；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人和日本人手里。有意思的是这两家都是国企，A公司在发展初期狠狠被德国人、日本人坑过，从董事长到技术骨干积攒了非常强烈的产业报国、技术报国的理想，从跟着日本人学、跟着德国人学，到越做越强、超越对手、对手跑过来跟他们学，再到做全产业链布局。如果你把这些东西全部写下来，就是一个产业上史诗般壮丽的东西，这种企业就是堪称伟大的企业。
+**主持人**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对于消费以外的行业选股，主要基于什么逻辑？
+**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的不可能三角、企业三阶段、三种商业模式。只不过消费行业基金只许买消费，不能买别的，所以肯定在消费行业里面选。两者的选股逻辑完全一样，没有什么区别。
+**主持人**：您是怎么看待血制品行业的竞争壁垒呢？
+**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开了，因为我们的研究不是特别深入。我们也找了一堆强壁垒的公司，相比之下买了另外的一些。
+**主持人**：在管理行业能否再具体讲一下呢？
+**肖楠**：就血制品这个行业，我们研究的不是特别多。我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有一些特别冲突的观点。
+**主持人**：农林牧渔行业有所提升，请问您对这个行业的观点能讲一下吗？
 **肖楠**：这行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。我们不能在公开场合讲具体股票的投资逻辑。农林牧渔行业的提升不是因为我先看好这个行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。
-**听众**：您能再具体讲一下生意模式里熵增和熵减的分析吗？
-**肖楠**：用直白的理论讲，你们都是企业里的打工人，能深切感受到：企业从小到大，部门越来越多，以前三五个部门现在十几个，中层干部一大堆，传达效率变低，内部腐败开始出现。企业为了解决这些问题又要设巡视检查部门，又多了部门，人还要加工资提级别。企业要扩张，往下游或上游做，又多一项业务，又要多一个副总裁和很多部门。有些生意收入10个亿和100个亿时没多几个部门，有些企业不需要设那么多高管就把生意做成了。从熵增角度讲，有些企业是熵增把自己拖死的。比如有些行业剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生，因为后者从一开始就没考虑好企业大了以后熵增怎么处理。而另一家基本是高度中央集权，CEO有非常强大的情报部门，知道每件重要事情细入基层是怎么回事。我特别建议大家去读一读党史，看看这个组织怎么从国民革命时期一直走到现在、到今天还能保证这样的活力，这是非常厉害的事情。有些国家也是被熵增拖死的，一条铁路修几十年这种事在很多国家都会发生。
-**听众**：您讲到伟大企业的增长曲线，能否再具体讲一下？
-**肖楠**：有些企业每年看都是线性增长，今年20%、明年15%、后年17.5%，但站到10年周期看，跟竞争对手之间拉开极大差距。比如快递，疫情的时候只有顺丰能送，没疫情时看不出来，一下子顺丰的业绩和估值把对手甩出一大截。家电领域也是，过去格力一直是老大，美的在做渠道扁平化、T+3，一直没看到成果，突然疫情来了，美的占有率一下子上去超过格力。当一些企业在埋头做事、还没体现到报表时，我们往往忽略这些事情未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的，平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞。
-**听众**：您讲到财富管理行业，能否具体展开讲一下投资逻辑和投资机会？
-**肖楠**：财富管理行业这个话题特别大，行业是分层的，顶级富豪、普通中产阶级、中低收入人员的财富管理意味着非常不同的事，有不同的公司和商业模式。我们最早关注这个行业是研究保险的时候，发现有些保险公司一个保险员一单能签七八千的首期保费，有些公司平均只有两三千，差距巨大。我们调研了特别厉害的销售和中等销售，发现同样是卖保险，背后的逻辑和机制差异超级大，这些公司的结构设置、激励机制、文化又有巨大差异。去年基金很火，我们发基金时发现，有些渠道经理过来调研问的问题超级专业，另外一些永远问下半年是涨是跌、明年是牛市还是熊市。财富管理行业最大的逻辑在于财富分布超级不均匀，会导致有些头部公司一口气拿掉行业增量的绝大部分，比如第一名拿掉70%、80%，第二名只能拿剩下20%的80%。在这种特别偏激、幂律分布的行业里，有可能诞生出特别大的企业。很遗憾，我们有一些产品因为监管和法律规则的原因反而不能投类似标的，但未来合同设置更清晰时，可能会在这方面有所体现。
-**听众**：您讲到第二第三增长曲线需要卓越的企业家精神，企业家精神是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
-**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营成功就说这个企业家特别厉害，就像不要因为一个基金经理业绩好就说他特别厉害。一定要把所有能归因到数据里客观指标的因素全部归因完，再特别谨慎地评价比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为企业家在所以公司就能值多少。我强调的一直是避免错误归因，避免因为对企业家认可去犯投资错误，一定要把底线风险搞好。我们一致同意这个东西不可被定价。这些比较虚的因素——技术进步、企业家精神——什么时候考虑？是在所有客观归因都尽量穷尽以后，可能某种程度上一些收益率的归因归到这里面去。另外，只能在有限范围内做两两比较，比如两家公司做同样生意、同样产品，在这种限定条件下比较两个企业家的水平高低、理念先后，去找你认可的那一家，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，要谨慎地用所谓企业家精神、伟大企业这些词，在一些特别极端的时候它可能是信仰上的支持，但尽量不要去用。</t>
+**主持人**：您能再具体讲一下生意模式里边商增和商减的分析吗？
+**肖楠**：用直白的理论讲，你们都是企业里的打工人，可以深切感受到：企业从小到大，部门越来越多，以前三五个部门现在十几个，中层干部一大堆，传达效率变低，内部腐败开始出现。企业为了解决这些问题又设巡视检查部门，部门里的人要加工资提级别，这么多部门老总今年提哪个明年提哪个，这些都是商增。企业扩张多一项业务就要多一个副总裁、多很多部门。有些生意收入10个亿和100个亿时没多几个部门，有些企业不需要设那么多高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如有些行业剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生，因为后者从一开始就没考虑好企业大了以后商增怎么处理。而另一家企业基本是高度中央集权，CEO有一个非常强大的情报部门，知道每一件重要事情细入到基层是怎么回事。我特别建议大家去读一读党史，看看这个国家怎么从国民革命时期、抗战时期一直走到现在，组织到今天还能保证这样的活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年这种事在很多国家都会发生。
+**主持人**：您讲到伟大企业的增长曲线，能否对这个曲线的情况再具体讲一下？
+**肖楠**：有些企业你每年看都是线性增长，今年增长20、明年15、后年17.5，但站到10年周期看，跟竞争对手之间拉开了极大差距。举个例子，快递行业，疫情的时候只有顺丰能送，没有疫情时你看不出来，一下子顺丰的业绩和估值把竞争对手甩出一大截。家电领域也是，过去格力一直是老大，美的在做渠道扁平化、T+3，一直没看到成果，突然疫情来了，美的占有率哗一下就上去了，超过了格力。当一些企业在埋头做事、还没体现到报表的时候，我们往往忽略这些事情未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的，平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞。
+**主持人**：由于时间关系，最后两个问题。您刚刚讲到财富管理行业，能否对这个行业具体展开，讲一下投资逻辑和投资机会？
+**肖楠**：财富管理行业这个话题特别大，行业是分层的，顶级富豪、普通中产阶级、中低收入人员的财富管理意味着非常不同的事，有不同的公司和商业模式。我们最早关注这个行业是研究保险的时候，发现某些保险公司一个保险员一单能签七八千的首年保费，有些公司平均一个业务员只有两三千的水平。我们调研了特别厉害的销售和中等销售，发现同样是卖保险，背后的逻辑和机制差异超级大，这些公司的结构设置、激励机制、文化又有巨大差异。去年基金非常火，我们发基金时发现，有些渠道经理过来调研问的问题超级专业，另外一些渠道经理永远问下半年是涨是跌、明年是牛市还是熊市。同样在这个行业混的人，经营结果差距巨大。财富管理行业最大的逻辑在于财富分布超级不均匀，所以有些头部公司真的一口气拿掉行业增量的绝大部分，可能拿掉70%、80%，第二名只能拿到剩下20%的80%。在这种特别偏激、幂律分布的行业里，有可能诞生出特别大的企业。很遗憾，我们有一些产品因为监管和法律规则的原因反而不能投类似标的，但未来合同设置更清晰的时候，我们可能会在这方面的投资上有所体现。
+**主持人**：您讲到第二第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
+**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营成功就说这个企业家特别厉害，就像不要因为一个基金经理业绩好就说他特别厉害。一定要把所有能归因到数据里客观指标的因素全部归因完，再特别谨慎地评价一些比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为这个企业家在，所以公司就能值多少。我强调的一直是避免错误归因，避免因为对企业家认可去犯投资错误，一定要把底线风险搞好。我们一致同意这个东西不可被定价。这些比较虚的因素——技术进步、企业家精神——什么时候考虑？在所有客观归因尽量穷尽以后，可能某种程度上一些收益率的归因要归到这里面去。另外，我们只能在有限范围内做两两比较，比如两家公司做同样生意、同样产品，在这种限定条件下比较两个企业家的水平高低、理念先后，去找你认可的那一家，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，一定要谨慎使用所谓企业家精神、伟大企业这些词，在一些特别极端的时候它可能是你某些信仰上的支持，但尽量不要去用。</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>87</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26252/7930</t>
+          <t>26252/8715</t>
         </is>
       </c>
     </row>
@@ -9218,51 +9247,40 @@
       <c r="C26" t="inlineStr">
         <is>
           <t># 辩论内容概述
-本次辩论赛围绕“拥有让人爱上自己的超能力是否美好”展开，正方为RUC棒辩论队，反方为另一支队伍。正方认为超能力是强行介入亲密关系、违背对方意志，类比强奸，因而不美好；反方则认为爱并非自由意志的产物，超能力机制未知，可能并非洗脑，因此美好。双方就超能力是否剥夺自由意志、是否等同于洗脑、爱情的本质与变质、超能力的使用与放手等议题展开交锋。正方在质询环节获胜，获得4分钟小结时间。
+本次辩论赛围绕“拥有让人爱上自己的超能力是否美好”展开，正方为RUC棒辩论队，反方为对方辩友。正方主张爱是自由意志的产物，超能力通过洗脑剥夺对方选择，类似占有而非爱；反方则认为爱非意志可控，超能力是改变自己或创造条件，且掌握在爱你的人手中优于未知命运。双方就超能力是否剥夺自由意志、是否等同于洗脑、真爱本质等核心议题展开交锋，正方在质询与自由辩论中逐步占据优势，最终评委判定正方获胜，获得4分钟小结时间。
 # 核心论点
-辩题为“拥有让人爱上自己的超能力是否美好”，正方主张不美好，反方主张美好。双方论点详见下表。
+辩题为“拥有让人爱上自己的超能力是否美好”，正方主张超能力剥夺自由意志、非真爱，反方主张爱非意志可控、超能力可改变自己或创造条件。双方论点详见下表。
 | 阵营 | 立论框架 | 核心论点 | 支撑论据 |
 | --- | --- | --- | --- |
-| 正方 | 超能力是强行介入亲密关系，违背对方意志，类比强奸 | 超能力剥夺自由意志 | 爱是相互付出；超能力使爱变质；应保留被爱者的选择空间 |
-| 正方 | 超能力使爱来得太容易，导致不珍惜 | 超能力使爱变质 | 珍惜程度取决于认真对待感情，而非获得爱的难易 |
-| 反方 | 爱并非自由意志的产物 | 爱不是自由意志的产物 | 如“坠入爱河”而非“跳入爱河”；超能力机制可能不是洗脑，而是改变自己或环境 |
-| 反方 | 爱是玄学，科学无法解释 | 爱是玄学 | 科学（如多巴胺）无法解释为何偏偏爱上某人；标准是为真爱打辅助 |
+| 正方 | 爱是自由意志的产物，超能力剥夺对方选择 | 超能力通过洗脑获取的爱是占有而非爱 | 类比强奸，违背对方意志强行介入亲密关系；真爱应保留对方说“不”的权利；超能力使爱来得太容易可能导致不珍惜 |
+| 反方 | 爱非意志可控，超能力可改变自己或创造条件 | 超能力可改变自己或创造100%符合对方需求的条件 | 爱是玄学，科学无法解释为何偏偏对某人产生爱；将红线交给爱你的人比交给未知命运更可靠 |
 # 环节交锋
-## 质询环节
-- 正方进攻：正方认为超能力是强行介入亲密关系，违背对方意志，类比强奸。反方回应：爱并非自由意志的产物，如“坠入爱河”而非“跳入爱河”，超能力机制可能不是洗脑，而是改变自己或环境。
-  &gt; “你方讲爱情这件事情里头没有100%的概率，其实意思是说，哪怕你长得再帅，总有人不喜欢你这一款。”
-- 正方进攻：正方质疑洗脑不是爱，且洗脑无法获得真爱。反方回应：超能力机制未知，可能改变自己而非洗脑，且爱是玄学，科学无法解释。
-  &gt; “洗脑错误，真的能够换回真爱，这个辩题在老师，用这个错误能力可能让你爱的人也。”
-- 正方进攻：正方认为超能力使爱来得太容易，导致不珍惜。反方回应：珍惜程度取决于认真对待感情，而非获得爱的难易，任何爱情都剥夺了其他可能性。
-  &gt; “难道我们在恋爱过程当中珍不珍惜对方这件事情完全看我们之间的新鲜感？”
-- 正方进攻：正方认为应保留被爱者的选择空间，使其有机会说不。反方回应：红线掌握在爱你的人手里比蒙眼小孩（月老）更好。
-  &gt; “我方认为掌握在一个爱你的人手里，比掌握在一个蒙眼的小孩子手里来的好的。”
-- 正方进攻：正方提出若相处后不合适应放手，反方质疑放手是否真爱。正方回应：若相处后不合适，会放手，但若一开始就做好放手准备，则不是真爱。
-  &gt; “如果这个时候真的是相处之后，我也觉得我跟他没有办法在一起，那这个时候爱的信号就是我会再用这个超能力。”
+## 开篇立论
+- **正方**：爱是自由意志的产物，超能力抹杀了对方的决定；月老和丘比特让有情人终成眷属，若强行牵线则非浪漫。
+- **反方**：爱是玄学，科学无法解释为何偏偏对某人产生爱；超能力可改变自己或创造100%符合对方需求的条件。
+## 质询
+- **正方**：超能力通过洗脑获取的爱是占有而非爱，类比强奸，违背对方意志强行介入亲密关系。
+- **反方**：爱非意志可控，超能力可改变自己或创造100%符合对方需求的条件，且掌握在爱你的人手中优于未知命运。
 ## 自由辩论
-- 正方进攻：正方认为超能力是洗脑，剥夺对方自由意志。反方回应：爱不是自由意志的产物，超能力机制可能不是洗脑。
-  &gt; “你方天然就认为你一定是通过洗脑来获取他的爱。第一个问题，洗脑真的是爱吗？”
-- 正方进攻：正方认为超能力使爱变质。反方回应：珍惜程度取决于认真程度，而非难易。
-  &gt; “我们最能够让爱保鲜的方式就是在恋爱过程当中相互忽略。”
-- 正方进攻：正方认为超能力剥夺了被爱者的选择空间。反方回应：应保留被爱者的选择空间，使其有机会说不。
-  &gt; “我们一定要保留一个希望，一定要保留一个被爱的那个人的选择空间，只要他有权利，他有余地，他有机会说不。”
+- **正方**：超能力使爱来得太容易，可能导致不珍惜；真爱应保留对方说“不”的权利。
+- **反方**：珍惜程度取决于认真对待，而非获得爱的难易；将红线交给爱你的人比交给未知命运更可靠。
+- **正方**：使用超能力后，若相处不合适应放手，否则留下遗憾。
+- **反方**：若一开始就做好可能不合适的准备，则放手是爱的表现。
 ## 小节总结
-- 正方总结：正方认为超能力是洗脑，剥夺自由意志，类比强奸；反方认为爱非自由意志产物，超能力机制未知。
-  &gt; “你方讲的所有的东西都是，当我要跟他发生性关系的时候，我要不要尊重他的意志，性关系和有没有爱是两回事。”
-- 反方总结：反方认为超能力可能改变自己而非洗脑，且爱是玄学，科学无法解释。
-  &gt; “科学已经显示了，为什么？是因为他。是爱情，但是特殊性无法解释，为什么我偏偏对他对他却不能产生。”
+- **正方**：反方未能论证爱是自由意志的产物，洗脑式获取的爱并非真爱，而是占有。
+- **反方**：将红线交给爱你的人比交给未知命运更可靠，保留被爱者的选择空间。
 # 结辩与评委点评
-- **正方结辩**：正方认为超能力是洗脑，剥夺自由意志，类比强奸，因而不美好。正方强调爱是相互付出，超能力使爱变质，应保留被爱者的选择空间。正方在质询环节获胜，获得4分钟小结时间。
-- **反方结辩**：反方认为爱非自由意志产物，超能力机制未知，可能改变自己而非洗脑。反方认为爱是玄学，科学无法解释，应保留被爱者的选择空间。
-- **评委点评**：评委未明示获胜方，但正方在质询环节获胜，获得4分钟小结时间。</t>
+- **正方结辩**：正方总结指出，反方未能论证爱是自由意志的产物，洗脑式获取的爱并非真爱，而是占有；真爱应保留对方说“不”的权利，超能力使爱来得太容易可能导致不珍惜。
+- **反方结辩**：反方强调爱是玄学，科学无法解释，超能力可改变自己或创造100%符合对方需求的条件，将红线交给爱你的人比交给未知命运更可靠。
+- **评委点评**：评委判定正方获胜，获得4分钟小结时间。</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>42.1</v>
+        <v>32.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12403/1906</t>
+          <t>12403/1264</t>
         </is>
       </c>
     </row>
@@ -9619,36 +9637,35 @@
       <c r="C27" t="inlineStr">
         <is>
           <t># 就诊概况
-患者为结肠癌术后转移患者，本次由家属陪同就诊，讨论后续治疗方案。患者于2023年9月因腹痛（疼了一晚上）确诊结肠癌，行结肠癌切除手术，术后完成8期化疗；复查发现肝转移，从老家来北京做PET-CT，去年9月行肝消融和乳腺结节切除，当时存在腹膜转移，肠切除可能不干净。消融和结节切除后行紫杉醇化疗，但仅第一次检查，后续因肝功能不行停用靶向药；3月底复查发现肝、肺、腹膜再次转移，4月份检查显示广泛转移。医生初步判断当前核心是全身系统治疗，建议进行基因检测与免疫评估，而非局部介入。
+患者为女性，年龄、职业未提及。2023年9月因腹痛确诊结肠癌并切除，术后行8期化疗；复查发现肝转移，行肝消融及乳腺结节切除，但腹膜转移可能切除不干净。后续化疗因肝功能不佳停用部分药物，停药3个月。2024年3月底复查发现肝、肺、腹膜转移，4月份PET-CT显示广泛转移，肠镜未见异常但PET显示有转移。本次就诊核心主诉为结肠癌术后转移，讨论后续全身治疗方案。
 # 病史与背景
-- **现病史**：2023年9月因腹痛（疼了一晚上）确诊结肠癌，行结肠癌切除手术，术后完成8期化疗。
-- **既往史**：多年来吃东西易中毒，如吃海鲜会上吐下泻，一直被认为肠胃比较弱。
-- **手术史**：结肠癌切除手术；去年9月行肝消融和乳腺结节切除；肠切除时可能切得不是特别干净，当时存在腹膜转移。
-- **转移情况**：术后复查发现肝转移，从老家来北京做PET-CT；3月底复查发现肝、肺、腹膜再次转移；4月份检查显示广泛转移，肝上、肺上、腹膜均有。
-- **近期用药**：消融和乳腺结节切除后行紫杉醇化疗，但仅第一次检查，后续因肝功能不行停用靶向药，中间停药3个月。
+- **现病史**：2023年9月因腹痛（疼了一晚上）确诊结肠癌，行结肠癌切除手术，术后行8期化疗；复查发现肝转移，行肝消融及乳腺结节切除，但腹膜转移可能切除不干净；后续化疗因肝功能不佳停用部分药物，停药3个月；2024年3月底复查发现肝、肺、腹膜转移；4月份PET-CT显示广泛转移，肠镜未见异常但PET显示有转移。
+- **既往史**：患者多年来肠胃较弱，吃海鲜易上吐下泻。
+- **手术史**：结肠癌切除手术、肝消融、乳腺结节切除。
+- **近期用药**：化疗药物（具体药名未提及），因肝功能不佳停用部分药物。
 # 诊断与检查结果
-- **诊断结论**：患者为结肠癌术后转移，当前存在肝、肺、腹膜广泛转移。
-- **检查结果**：PET-CT显示肝转移；4月份检查显示广泛转移；上个月肠镜显示没事，但PET显示有问题，医生认为可能是肠镜做得不好。
-- **基因检测**：医生建议做基因检测，特别是针对转移灶的二次检测，以提高检出率；检测可通过血液、尿液、唾液等进行。
-- **免疫评估**：医生强调免疫细胞状态重要，数量不足需提升质量；建议做免疫评估，但方案由患者决定。
+- **诊断结论**：结肠癌术后转移，累及肝、肺、腹膜。
+- **检查结果**：4月份PET-CT显示广泛转移；肠镜显示无异常，但PET显示有转移，医生认为可能是肠镜做得不好。
+- **基因检测**：建议进行基因检测（包括M2D等），可通过组织、血液、尿液、唾液进行。
+- **免疫评估**：建议进行免疫评估，了解免疫细胞状态。
 # 治疗方案与医嘱
-- **全身系统治疗**：医生强调当前核心是全身系统治疗，包括化疗、靶向、免疫，局部介入（如肝消融）不是当前主要问题；若肿瘤增长至10公分或危及生命，才考虑局部处理。
-- **基因检测**：建议进行基因检测，特别是针对转移灶的二次检测，以提高检出率；检测可通过血液、尿液、唾液等进行。
-- **免疫评估**：建议做免疫评估，但方案由患者决定。
-- **生活方式**：建议患者提升免疫力，调整好状态。
-- **复诊与陪同**：患者今早查了血。
-| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
-| --- | --- | --- | --- | --- |
+- **检查安排**：建议进行基因检测（包括M2D等），可在肿瘤医院进行；建议进行免疫评估。
+- **治疗建议**：当前主要问题是全身系统治疗（化疗、靶向、免疫可联合使用），而非局部介入；若肿瘤增大至10公分或危及生命，才需考虑局部处理。
+- **用药说明**：因肝功能不佳，化疗药物停用部分，停药3个月。
+- **生活方式**：建议患者调整状态，提升免疫力。
+| 药品名称 | 用法用量 | 注意事项 |
+| --- | --- | --- |
+| 未提及 | — | — |
 # 复诊与预警信号
 未提及</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>115.8</v>
+        <v>26.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7063/1089</t>
+          <t>7063/897</t>
         </is>
       </c>
     </row>
@@ -9811,44 +9828,44 @@
       <c r="C28" t="inlineStr">
         <is>
           <t># 产品概况
-海尔洗衣机创新发布会正式推出洗干集成新物种迭代H2，由海尔打造，专为中国家庭设计。发布会以「纯净永无止境」为主题，强调「洗干集成新物种」的诞生。针对中国80%用户将洗烘套装叠放于阳台使用的现状，迭代H2专为客阳一体空间设计，采用一体集成机身，解决叠放带来的震动等安全隐患，高度降至167厘米，可嵌入60厘米标准橱柜。目标人群为向往整洁有序新阳台的中国家庭，尤其是年轻人与养宠、有宝宝的家庭。主要目标是让用户告别晾晒与繁琐家务，享受整洁有序的家居生活。
+海尔洗衣机创新发布会于海尔洗衣机用户研发中心举行，主讲人介绍了专为中国用户阳台叠放痛点设计的洗干集成新物种迭代H2。该产品一体集成机身，解决洗烘套装叠放带来的震动安全隐患，高度降至167厘米，超薄机身可嵌入60厘米标准橱柜，全平不突出，并采用同向开门与无水盒设计。H2搭载多项创新技术：灵犀洗烘联动实现数据共享，洗涤结束前上桶提前15分钟主动预热；原创双擎热泵技术使大件烘干不缠绕；首次引入3D透视烘干，羽绒服和水洗被可一次烘透；升级精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗减少洗衣液残留；空净过滤系统去除衣物线屑和毛絮；三台变频电机降低洗涤、甩干、烘干全过程噪音。两款产品定价公布：10kg 3D透视烘干款12998元，10kg净净双擎热泵款10998元。
 # 市场定位与目标用户
-目标人群为中国家庭，尤其是年轻人、养宠家庭和有宝宝的家庭。典型使用场景为客阳一体风格的阳台，用户在此休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间。市场背景方面，欧洲家庭有独立洗衣房，洗烘套装并排摆放；中国80%用户将洗烘套装叠放在阳台使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便。迭代H2针对这一差异，以一体集成机身、无水盒设计、同向开门等解决痛点，定位为客阳一体空间的黄金选择。
+目标人群为中国家庭，尤其是追求整洁有序新阳台、希望从漫长家务中解放出来的年轻人，以及养宠物、有宝宝的家庭。典型使用场景为客阳一体风格的阳台，用户在此休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间。市场背景：在欧洲滚筒洗衣机发源地，许多家庭有独立洗衣房，洗烘套装并排摆放；而在中国，80%的用户把洗烘套装叠放在阳台使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便。产品专为客阳一体空间设计，一体集成机身解决叠放带来的震动等安全隐患，高度降为167厘米，超薄机身嵌入60厘米标准橱柜，全平不突出，同向开门尊重使用习惯，无水盒设计无需手动倒水。
 # 核心卖点与技术参数
-## 一体集成设计
-- **一体集成机身**：解决洗烘套叠放带来的震动等安全隐患，高度降为167厘米，不用踮脚即可操作。
-- **超薄机身**：完美嵌入60厘米标准橱柜，全平不突出，让阳台更美观整洁。
-- **同向开门**：尊重使用习惯，取放衣物流畅自如。
-- **无水盒设计**：无需手动倒水。
+## 集成设计
+- **一体集成机身**：专为客阳一体空间设计，解决洗烘套叠放带来的震动等安全隐患，高度降为167厘米，不用踮脚尖即可操作
+- **超薄平嵌**：超薄机身完美嵌入60厘米标准橱柜，全平不突出，让阳台更美观整洁
+- **同向开门**：尊重使用习惯，取放衣物流畅自如
+- **无水盒设计**：无需手动倒水
 ## 智慧互联
-- **灵犀洗烘联动**：实现数据共享，洗涤结束前上桶提前15分钟主动预热，缩短烘干时长。
-- **智慧大脑**：以屏幕为核心，全面操控洗涤、烘干和护理等多种模式，利用中枢神经式智能网络让上下桶默契配合。
+- **灵犀洗烘联动**：H2独有的灵犀洗烘联动实现数据共享，让烘干和洗涤无缝连接，洗涤结束前上桶提前15分钟主动预热，缩短烘干时长
+- **智慧大脑**：H2全新升级的智慧大脑，利用中枢神经式的智能网络，让上下桶默契配合
 ## 烘干技术
-- **原创双擎热泵技术**：大件烘干不缠绕。
-- **3D透视烘干**：行业领先黑科技，羽绒服、水洗被可一次烘透，免去二次晾晒。
+- **原创双擎热泵技术**：大件烘干不缠绕
+- **3D透视烘干**：首次引入行业领先黑科技，羽绒服和水洗被可一次烘透，免去二次晾晒烦恼
 ## 洗涤技术
-- **精华洗2.0**：激活洗衣液，39分钟洗净一周衣物。
-- **新鲜净水漂洗**：减少洗衣液残留，对残留泡沫敏感人群友好。
-## 健康与静音
-- **空净过滤系统**：去除衣物线屑和毛絮，适合养宠家庭，洗衣无残留、干衣无毛絮。
-- **三台变频电机**：洗涤、甩干、烘干全过程噪音低。
+- **精华洗2.0**：升级精华洗2.0，激活洗衣液39分钟洗净一周衣物
+- **新鲜净水漂洗**：减少洗衣液残留，对残留泡沫敏感的人是福音
+## 健康护理
+- **空净过滤系统**：去除衣物线屑和毛絮，适合养宠物的家庭，洗衣无残留、干衣无毛絮，特别适合有宝宝的家庭
+- **三台变频电机**：洗涤、甩干、烘干全过程噪音低，享受安静陪伴时光
 | 维度 | 本产品 | 上代/竞品 | 提升 |
 | --- | --- | --- | --- |
-| 一体集成设计 | 一体集成机身，高度167厘米，嵌入60厘米橱柜，无水盒设计，同向开门 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决震动安全隐患，操作更便捷，外观更整洁 |
-| 智慧互联 | 灵犀洗烘联动，上桶提前15分钟预热 | 洗烘套装貌合神离，无联动 | 烘干与洗涤无缝连接，缩短烘干时长 |
-| 烘干技术 | 原创双擎热泵技术，3D透视烘干 | 未提及 | 大件不缠绕，羽绒服、水洗被一次烘透 |
-| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗 | 未提及 | 洗衣高效，减少洗衣液残留 |
-| 健康与静音 | 空净过滤系统，三台变频电机 | 未提及 | 去除线屑毛絮，全过程噪音低 |
+| 集成设计 | 一体集成机身，高度167厘米，超薄嵌入60厘米标准橱柜，全平不突出，同向开门，无水盒设计 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决震动安全隐患，操作更便捷，阳台更美观整洁 |
+| 智慧互联 | 灵犀洗烘联动，数据共享，洗涤结束前上桶提前15分钟主动预热 | 洗烘套装貌合神离，无联动 | 烘干和洗涤无缝连接，缩短烘干时长 |
+| 烘干技术 | 原创双擎热泵技术，大件烘干不缠绕；首次引入3D透视烘干，羽绒服和水洗被一次烘透 | 未提及 | 免去二次晾晒烦恼 |
+| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物；新鲜净水漂洗减少洗衣液残留 | 未提及 | 洗衣更高效，减少残留 |
+| 健康护理 | 空净过滤系统去除线屑毛絮；三台变频电机降低噪音 | 未提及 | 适合养宠和有宝宝家庭，安静陪伴 |
 # 定价与发售信息
-10kg 3D透视烘干款定价12998元，10kg净净双擎热泵款定价10998元。定价策略为「诚意满满的定价」，针对平嵌超薄产品。发售时间、购买渠道与预售政策未提及。</t>
+10kg 3D透视烘干款定价12998元，10kg净净双擎热泵款定价10998元。定价策略：海尔为这款平嵌超薄产品拿出诚意满满的定价。发售时间、购买渠道与预售政策未提及。</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>30.6</v>
+        <v>33.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7311/1414</t>
+          <t>7311/1702</t>
         </is>
       </c>
     </row>
@@ -10051,110 +10068,90 @@
       <c r="C29" t="inlineStr">
         <is>
           <t># 全文摘要
-中共巢湖市银屏镇白母山村芦塘支部召开党员大会改选支部委员会，支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数；银屏镇党委组织委员钱小丽应邀到会并讲话。会议围绕换届选举展开，依次完成上届支部委员会工作报告审议、选举办法通过、候选人名单确认、竞职演说、无记名投票选举委员及书记、委员分工等议程。经投票，卢燕娇、辛东升、杜军强当选新一届支部委员会委员，卢燕娇以3票当选支部书记，辛东升负责组织宣传、杜军强负责纪检工作，最终结果以报镇党委批准为准。关键数字：支部正式党员8名、实到7名；上届收缴党费2640元上交上级党组织；委员候选人4名差额1名、应选3名；卢燕娇、杜军强各得6票，秦磊2票。
+中共巢湖市银屏镇白母山村芦塘支部召开党员大会改选支部委员会。支部共有正式党员8名，因病请假1名，实到会有选举权党员7名，符合法定人数；银屏镇党委组织委员钱小丽应邀出席并代表镇党委提出三点意见。会议围绕换届选举展开，依次完成上届支部委员会工作报告审议、通过大会选举办法、支委候选人名单及监票计票人员名单、候选人竞职演说、无记名投票选举新一届支部委员和书记、支委分工等议程。大会选举发出并收回选票7张，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员；第一次支委会发出并收回选票3张，卢燕娇以3票当选党支部书记，辛东升负责组织宣传工作、杜军强负责纪检工作，最终结果以报镇党委批准为准。上届工作报告提及三年间新发展党员1名、收缴党费2640元上交上级党组织。
 # 分段速览
-## 00:00:13-00:02:03 会议开始与奏国歌
-主持人宣布召开中共巢湖市银屏镇白母山村芦塘支部党员大会，改选支部委员会。支部共有党员8名，其中正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。银屏镇党委组织委员钱小丽应邀参会，全体起立奏国歌。
-## 00:02:15-00:05:12 镇党委讲话与上届工作报告
-钱小丽代表镇党委就换届选举提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局遵守选举纪律。主持人代表上届支部委员会作工作报告，总结三年工作，涵盖思想政治建设、党支部建设、主题教育活动、党务公开、党风党纪教育等方面，同时指出党建工作制度不够完善、党员主体意识尚需提高、对党员教育管理监督不够深入等问题。
-## 00:05:19-00:05:55 讨论通过工作报告
-与会党员对工作报告进行讨论，党员表示报告非常好、非常满意，无其他意见，鼓掌通过。
-## 00:05:55-00:08:39 通过大会选举办法
-杜军晓宣读党员大会选举办法草案，规定选举支部委员3名、候选人4名，差额不少于应选名额20%，采用无记名投票，先差额选举委员再等额选举书记。与会党员表决一致通过。
-## 00:08:39-00:10:43 通过候选人名单与工作人员名单
-杜军晓宣读镇党委批复，同意新一届支部委员会委员候选人预备人选4名（卢燕娇、辛东升、杜军强、秦磊），书记候选人预备人选为卢燕娇，批复日期2019年10月12日。与会党员鼓掌通过候选人名单。提议贾淑玲担任监票人，黄婷丽、刘彩云为计票人员，表决通过。
+## 00:00:13-00:02:03 大会开幕
+主持人宣布召开中共巢湖市银屏镇白母山村芦塘支部党员大会，改选支部委员会。支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到会有选举权党员7名，符合法定人数。银屏镇党委组织委员钱小丽应邀参加。主持人宣布大会开始，全体起立奏国歌。
+## 00:02:03-00:05:12 领导讲话与工作报告
+钱小丽代表镇党委提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。主持人代表上届支部委员会作工作报告，总结三年工作：加强思想政治建设和理论学习、抓好党支部建设、开展主题教育活动、党务公开、党风党纪教育；新发展党员1名，按规定收缴党费2640元上交上级党组织。报告指出存在问题：党建工作制度不够完善、党员主体意识尚需提高、党支部对党员教育管理监督不够深入。
+## 00:05:12-00:08:39 通过选举办法
+党员对工作报告无意见，鼓掌通过。杜军晓宣读党员大会选举办法草案，规定：选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；无记名投票，先差额选举委员再等额选举书记；实到会有选举权党员须超过应到会4/5方可选举；收回选票数等于或少于发出选票数选举有效；候选人得赞成票超过应到会选举人数半数方可当选。党员一致通过。
+## 00:08:39-00:10:43 通过候选人及工作人员名单
+杜军晓宣读镇党委批复，同意委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇，批复日期2019年10月12日。党员无不同意见，鼓掌通过。提议贾淑玲担任监票人，表决通过；宣布计票人员为黄婷丽、刘彩云。
 ## 00:10:43-00:14:45 候选人竞职演说
-四位候选人依次发表竞职演说。卢燕娇承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强承诺担当桥梁纽带角色，为党员和群众服务；辛东升承诺群众有困难随叫随到，严格要求自己，完成上级任务；秦磊承诺有责任心、思想觉悟高，配合上级工作，不计较个人得失。
-## 00:14:45-00:21:17 大会选举新一届支部委员会
-清点人数确认实到有选举权党员7名，达到应到会人数4/5要求。发出选票7张，收回选票7张，选举有效。计票结果：卢燕娇6票，杜军强6票，秦磊2票。卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。
+四位候选人依次演说。卢燕娇（1993年9月出生，2014年4月入党）承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强承诺担当桥梁纽带角色，为党员和群众服务；辛东升承诺群众有困难随叫随到，严格要求自己，完成上级任务；秦磊承诺有责任心、思想觉悟高，配合上级工作，不计较个人得失。
+## 00:14:45-00:21:17 大会选举新一届支部委员
+清点人数：应到会有选举权党员8名，因病请假1名，实到7名，达到应到会4/5，可以进行选举。检查票箱、分发选票、说明填写方法后投票。实到会有选举权党员7名，发出选票7张，收回7张，选举有效。计票结果：卢燕娇6票、杜军强6票、秦磊2票。卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。
 ## 00:21:17-00:28:42 第一次支委会选举书记及分工
-新当选委员召开第一次支部委员会全体会议，通过选举办法，选举产生支部书记。发出选票3张，收回选票3张，卢燕娇以3票当选为新一届党支部书记。分工为：辛东升负责组织宣传工作，杜军强负责纪检工作。大会宣布选举结果，最终结果以报镇党委批准为准。
-## 00:28:42-00:29:56 新当选代表发言与大会结束
-新当选支委代表发言，承诺抓好支部学习工作、制度建设工作、完善基层党组织建设。大会宣布换届选举大会圆满结束，全体起立奏国际歌。
+新当选委员召开第一次支委会，通过选举办法，规定等额选举书记1人，实到会委员须超过应到会4/5方可选举。主持人建议卢燕娇继续担任支部书记，无不同意见，鼓掌通过；提议辛东升担任监票人和计票人，表决通过。发出选票3张，收回3张，卢燕娇得3票当选新一届党支部书记。分工：辛东升负责组织宣传工作，杜军强负责纪检工作。
+## 00:28:42-00:29:56 宣布结果及闭幕
+主持人宣布选举结果：卢燕娇当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。新当选支委代表发言，承诺抓好学习、制度建设、完善基层党组织建设。大会圆满结束，全体起立奏国际歌。
 # 要点梳理
-## 会议开场与出席情况
-- **会议性质**：中共巢湖市银屏镇白母山村芦塘支部党员大会，改选中共巢湖市银屏镇白母山村芦塘支部委员会。
-- **党员人数**：支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到有选举权党员7名，符合法定人数。
-- **列席人员**：银屏镇党委组织委员钱小丽同志应邀参加。
-- **会议程序**：宣布大会开始，全体起立奏国歌；钱小丽代表镇党委讲话。
-## 镇党委组织委员讲话
-- **钱小丽**代表镇党委就换届选举工作提三点意见：充分认识这次大会的重要意义；正确行使选举权，严格把握选举要求；服从大局，严格遵守选举纪律。
-- **钱小丽**希望新一届班子加强学习、提高素质，发挥战斗堡垒作用，带领全村党员和群众将白母山村建设得更加美好。
+## 换届选举大会开幕及领导讲话
+- **参会人数**：支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到会有选举权党员7名，符合法定人数。
+- **出席人员**：银屏镇党委组织委员钱小丽应邀参加。
+- **钱小丽讲话**：代表镇党委提出三点意见——充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。
 ## 上届支部委员会工作报告
-- **报告人**：上届支部委员会受芦塘党支部委托作工作报告，请同志们审议。
-- **三年工作总结**：在上级党组织领导和关怀下，团结带领支部全体党员，认真落实党建工作各项要求，发挥党支部战斗堡垒作用和党员模范带头作用。
-- **思想政治建设**：大力加强思想政治建设和理论学习，努力提高党员干部的思想理论水平。
-- **党支部建设**：严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度；新发展党员1名；按规定收缴党费2640元上交上级党组织。
-- **主题教育活动**：扎实开展“两学一做”学习教育常态化、制度化和“讲严立”专题警示教育活动等。
-- **党务公开**：将年度工作计划、党风廉政建设、党费收缴等内容，通过党内会议、公开栏等形式进行公开。
-- **党风党纪教育**：认真抓好党风党纪教育，筑牢拒腐防变的思想防线，落实党风廉政建设各项责任。
-- **存在问题**：党建工作制度还不够完善；党员主体意识尚需进一步提高，个别党员干部围绕中心服务大局的意识还不强；党支部对党员的教育管理监督还不够深入。
-- **讨论与表决**：党员发言表示报告非常好、非常满意；无其他意见，鼓掌通过。
-## 通过党员大会选举办法
-- **宣读人**：杜军晓宣读《中国共产党芦塘支部党员大会选举办法（草案）》。
-- **委员名额与差额**：大会选举中共芦塘支部委员会委员3名；候选人差额不少于应选名额20%，确定委员候选人4名。
-- **候选人排序与投票方式**：候选人按姓氏笔画为序排列；选举采用无记名投票方式。
-- **候选人产生程序**：候选人建议名单在征求多数党员意见基础上，由本届支部研究提名，镇党委考察并批准后确定，提交大会选举。
-- **选举步骤**：先差额选举支部委员会委员，再从当选委员中等额选举书记；两次选举分别投票、计票和宣布选举结果。
-- **有效条件**：参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；收回选票数等于或少于发出选票数选举有效，多于发出选票数选举无效应重新选举。
-- **当选规则**：候选人得到赞成票数超过应到会选举人数的半数方可当选；得票超过半数的候选人多于应选名额时以得票多少为序取足应选名额；最后几名候选人得票相等时在票数相等者中重新投票；得票超过半数的候选人少于应选名额时，不足名额在得票未超过半数的候选人中重新选举产生，接近应选名额也可减少名额不再选举。
-- **选票填写**：投赞成票在候选人姓名上方空格内画圈，投不赞成票画叉，弃权不画任何符号；另选他人在候选人后面空格内写另选人姓名并在其姓名上方空格内画圈，只写姓名不画圈无效；每张选票所选人数等于或少于应选人数有效，超过应选人数无效。
-- **工作人员**：设监票人1名经大会表决通过，设选举工作人员2名由会议主持人指定，在监票人监督下工作；被提名为支部委员候选人的不能担任监票人和工作人员。
-- **表决结果**：无不同意见，一致通过选举办法。
+- **工作成绩**：三年工作总结为五个方面——加强思想政治建设和理论学习、抓好党支部建设增强凝聚力、开展主题教育活动改进思想作风、开展党务公开推进党内民主、抓好党风党纪教育筑牢拒腐防变思想防线。
+- **具体数据**：新发展党员1名，按规定收缴党费2640元上交上级党组织。
+- **存在问题**：党建工作制度不够完善；党员主体意识尚需提高，个别党员干部顶推中心服务大局的意识不强；党支部对党员教育管理监督不够深入。
+- **报告审议**：党员对报告无意见，鼓掌通过。
+## 通过大会选举办法
+- **选举办法要点**：大会选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；候选人按姓氏笔画为序排列。
+- **选举方式**：采用无记名投票，先差额选举支部委员会委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布结果。
+- **有效条件**：参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；收回选票数等于或少于发出选票数选举有效，多于则无效。
+- **当选规则**：候选人得到赞成票数超过应到会选举人数半数方可当选；得票超过半数的候选人多于应选名额时以得票多少为序取足；最后几名票数相等时重新投票；超过半数候选人少于应选名额时不足名额在未过半数候选人中重新选举，接近应选名额可减少名额不再选举。
+- **选票填写**：赞成在候选人姓名上方空格画圈，不赞成画叉，弃权不画符号；另选他人在候选人后面空格写姓名并在其姓名上方画圈，只写姓名不画圈无效；每张选票所选人数等于或少于应选人数有效，超过无效。
+- **工作人员**：设监票人1名经大会表决通过，设选举工作人员2名由会议主持人指定；支部委员候选人不能担任监票人和工作人员。
+- **表决结果**：杜军晓宣读选举办法草案，党员大会一致通过。
 ## 通过支委候选人名单
-- **批复宣读**：杜军晓宣读《银屏镇党委关于同意中共巢湖市银屏镇白母山村芦塘支部委员会组成人员候选人预备人选的批复》。
-- **批复内容**：同意新一届芦塘支部委员会委员和书记候选人预备人选名单；委员实行差额选举，差额1人；书记实行等额选举。
-- **委员候选人预备人选4名**：卢燕娇、辛东升、杜军强、秦磊。
-- **书记候选人预备人选**：卢燕娇。
-- **批复日期**：2019年10月12日，中共巢湖市银屏镇委员会。
-- **表决结果**：无不同意见，鼓掌通过候选人名单。
+- **镇党委批复**：银屏镇党委批复同意新一届支部委员会委员和书记候选人预备人选名单，批复日期2019年10月12日。
+- **候选人名单**：委员候选人预备人选4名——卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇。
+- **选举方式批复**：委员实行差额选举，差额1人；书记实行等额选举。
+- **表决结果**：党员无不同意见，鼓掌通过候选人名单。
 ## 通过选举工作人员名单
-- **监票人**：提议贾淑玲同志担任监票人。
-- **计票人员**：黄婷丽、刘彩云。
-- **表决结果**：无意见，一致通过监票人建议名单。
+- **监票人**：提议贾淑玲担任监票人，经表决一致通过。
+- **计票人**：宣布计票人员为黄婷丽、刘彩云。
 ## 候选人竞职演说
-- **卢燕娇**：1993年9月出生，2014年4月加入中国共产党；承诺进一步加强支部建设，落实“三会一课”、组织生活会和民主评议党员等基本制度，结合“两学一做”学习教育常态化制度化扎实开展“不忘初心、牢记使命”主题教育；进一步推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领和帮扶帮带作用；进一步抓好各项民生工程落实，把群众利益作为工作首要职责，把群众满意度作为衡量工作标准。
-- **杜军强**：从事村委会工作，是基层党组织与党员群众之间的桥梁和纽带；承诺如果成为支部委员，更好担当主导角色，为党员和群众服务。
+- **卢燕娇**：1993年9月出生，2014年4月加入中国共产党；承诺进一步加强支部建设，落实三会一课、组织生活会和民主评议党员等基本制度，结合两学一做学习教育常态化制度化开展不忘初心、牢记使命主题教育；进一步推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领和帮扶帮带作用；进一步抓好各项民生工程落实，把群众利益作为工作首要职责、群众满意度作为衡量工作标准。
+- **杜军强**：从事村委会工作，平时与各类人群有工作接触；承诺如当选可更好担当桥梁纽带角色，向基层党员传达广大党员和群众的利益诉求，为党员和群众服务。
 - **辛东升**：承诺群众有困难随叫随到；严格要求自己做合格党员干部，不该吃的饭不吃、不该拿的钱不拿、不该做的事不做；圆满完成上级党组织分配的各项任务。
-- **秦磊**：竞选有利条件为有较强责任心，能认真参加支部组织的理论学习，不折不扣完成组织交给的任务；有较高思想觉悟，积极参加学习，热情为群众办实事；承诺配合上级各项工作，全体党员团结一心，听从大局，不计较个人得失，当一名合格的支部委员。
-## 大会选举新一届支部委员会
-- **人数清点**：中共芦塘支部委员会应到会有选举权党员8名，因病请假1名，实到7名，达到应到会有选举权党员人数的4/5，可以进行选举。
-- **选票发放与回收**：监票人员检查并封好票箱，领取并分发选票；实到有选举权党员7名，发出选票7张，收回选票7张，选举有效。
-- **填写说明**：对候选人可投赞成票、不赞成票、弃权或另选他人；每张选票所选人数等于或少于应选人数为有效票，多于应选人数为无效票；填写选票一律用钢笔，字迹要清楚。
-- **投票顺序**：先由监票人员、计票人员投票，然后全体党员依次投票。
+- **秦磊**：竞选有利条件为有较强责任心、能认真参加支部组织的理论学习、不折不扣完成组织交给的任务；有较高思想觉悟，利用业余时间学习；承诺配合上级和各项工作，全体党员团结一心，不计较个人得失，当一名合格的支部委员。
+## 大会选举新一届支部委员
+- **清点人数**：应到会有选举权党员8名，因病请假1名，实到会7名，达到应到会有选举权党员人数的4/5，可以进行选举。
+- **选票发放与回收**：发出选票7张，收回选票7张，选举有效。
 - **计票结果**：卢燕娇6票，杜军强6票，秦磊2票。
-- **当选结果**：根据大会选举办法规定，卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。
-## 第一次支部委员会全体会议选举书记及分工
-- **会议内容**：宣读《中共巢湖市银屏镇白母山村芦塘支部委员会第一次全体会议选举办法（草案）》；选举新一届党支部书记；对支委会委员进行分工。
-- **选举办法要点**：选举产生支部书记1人；候选人建议名单由上届支部委员会根据镇党委批复提交新选举产生的支委会第一次全体会议酝酿，根据多数委员意见确定正式候选人；采用无记名投票方式，书记采用等额选举；实到会委员必须超过应到会委员的4/5方可选举；收回选票等于或少于发出选票选举有效；候选人得赞成票超过实到会委员半数当选；设监票人1名由会议主持人在不是书记候选人的人员中提名，计票人由会议主持人指定。
-- **书记候选人建议名单**：卢燕娇同志工作认真负责，上届支委会在其带领下各项工作取得较好成绩，建议继续由卢燕娇同志担任支部书记；无不同意见，鼓掌通过。
-- **选举工作人员**：提议辛东升同志担任监票人和计票人；无意见，一致通过。
-- **选举结果**：发出选票3张，收回选票3张；卢燕娇3票，当选为新一届党支部书记。
-- **委员分工**：辛东升同志负责组织宣传工作，杜军强同志负责纪检工作；无意见，明确分工。
-## 宣布选举结果及新当选代表发言
-- **大会宣布**：根据大会选举办法规定，卢燕娇同志当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。
-- **新当选支委代表发言**：代表新当选的三位支部委员感谢各位领导和党员的信任与支持；承诺下一步抓好支部学习工作，争创学习型支部，认真组织开展“不忘初心、牢记使命”主题教育；抓好支部制度建设工作，争创制度型支部，增强党支部凝聚力、战斗力；完善基层党组织建设，争创服务型支部，严格按照《中国共产党支部工作条例（试行）》加强支部建设，发挥党支部战斗堡垒和党员先锋模范作用，更好服务基层、服务群众。
-- **大会结束**：宣布中共巢湖市银屏镇白母山村芦塘支部委员会换届选举大会圆满结束，全体起立奏国际歌。
+- **当选结果**：卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。
+## 第一次支委会选举书记及分工
+- **选举办法**：支委会第一次全体会议选举产生支部书记1人；选举工作由上届支部委员会委托一名新当选委员主持；书记候选人建议名单由上届支委会根据镇党委批复提交新支委会酝酿，根据多数委员意见确定正式候选人；采用无记名投票，等额选举；实到会委员须超过应到会委员4/5方可选举；候选人得赞成票超过实到会委员半数当选。
+- **书记候选人**：主持人介绍卢燕娇工作认真负责，上届支委会在其带领下各项工作取得较好成绩，建议继续由卢燕娇担任支部书记；无不同意见，鼓掌通过。
+- **工作人员**：提议辛东升担任监票人和计票人，表决通过。
+- **选举结果**：发出选票3张，收回选票3张，卢燕娇得3票当选新一届党支部书记。
+- **委员分工**：辛东升负责组织宣传工作，杜军强负责纪检工作。
+## 宣布选举结果及闭幕
+- **选举结果宣布**：卢燕娇当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。
+- **新当选支委代表发言**：承诺抓好支部学习工作，争创学习型支部，组织开展不忘初心、牢记使命主题教育；抓好支部制度建设工作，争创制度型支部；完善基层党组织建设，争创服务型支部，严格按照中国共产党党支部工作条例（试行）加强支部建设，发挥战斗堡垒和党员先锋模范作用。
+- **大会闭幕**：大会完成各项任务，全体起立奏国际歌，换届选举大会圆满结束。
 ## 结论与决定
-- **通过上届支部委员会工作报告**：党员发言表示报告非常好、非常满意，无其他意见，鼓掌通过。
-- **通过党员大会选举办法**：无不同意见，一致通过。
-- **通过支委候选人名单**：卢燕娇、辛东升、杜军强、秦磊，鼓掌通过。
-- **通过选举工作人员名单**：监票人贾淑玲，计票人员黄婷丽、刘彩云，一致通过。
-- **选举产生新一届支部委员会委员**：卢燕娇、辛东升、杜军强当选，依据计票结果（卢燕娇6票、杜军强6票、秦磊2票）。
-- **选举产生新一届党支部书记**：卢燕娇以3票当选，最终结果以报镇党委批准为准。
-- **支委会委员分工**：辛东升负责组织宣传工作，杜军强负责纪检工作。
+- **通过党员大会选举办法**：党员大会一致表决通过。
+- **通过支委候选人名单**：卢燕娇、辛东升、杜军强、秦磊为委员候选人，卢燕娇为书记候选人，鼓掌通过。
+- **通过选举工作人员名单**：贾淑玲任监票人，黄婷丽、刘彩云任计票人，表决通过。
+- **新一届支部委员会当选**：卢燕娇、辛东升、杜军强当选为支部委员会委员。
+- **新一届党支部书记当选**：卢燕娇当选为党支部书记，等额选举得3票，最终结果以报镇党委批准为准。
+- **委员分工确定**：辛东升负责组织宣传工作，杜军强负责纪检工作。
 ## 行动项与分工
-- **辛东升**：负责新一届支部委员会组织宣传工作。
-- **杜军强**：负责新一届支部委员会纪检工作。
-- **选举结果报批**：选举结果报镇党委批准，最终结果以批准为准。</t>
+- **辛东升**：负责支部组织宣传工作。
+- **杜军强**：负责支部纪检工作。
+- **新一届支委会**：抓好支部学习工作，组织开展不忘初心、牢记使命主题教育；抓好支部制度建设工作；完善基层党组织建设，按中国共产党党支部工作条例（试行）加强支部建设。
+- **选举结果报送**：选举结果报镇党委批准（原文明确最终结果以报镇党委批准为准，未明确具体报送时限与责任人）。</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>70.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8414/5594</t>
+          <t>8414/4684</t>
         </is>
       </c>
     </row>
@@ -10291,140 +10288,131 @@
       <c r="C30" t="inlineStr">
         <is>
           <t># 报告概况
-本报告为国务院总理代表国务院在第十四届全国人民代表大会第二次会议上所作的《政府工作报告》，发布单位为国务院，报告期间涵盖2023年工作回顾与2024年工作部署。报告核心主题是全面贯彻党的二十大精神，回顾2023年经济社会发展成绩，提出2024年经济社会发展总体要求、主要预期目标和政府工作任务，整体基调为坚持稳中求进、以进促稳、先立后破，巩固和增强经济回升向好态势，以中国式现代化全面推进强国建设、民族复兴伟业。报告指出，2023年面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务，全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元、增长5.2%，城镇新增就业1244万人，粮食产量1.39万亿斤再创历史新高；2024年主要预期目标为国内生产总值增长5%左右、城镇新增就业1120万人以上、居民消费价格涨幅3%左右，并部署了大力推进现代化产业体系建设、深入实施科教兴国战略、着力扩大国内需求、坚定不移深化改革、扩大高水平对外开放、更好统筹发展和安全、坚持不懈抓好三农工作、推动城乡融合和区域协调发展、加强生态文明建设、切实保障和改善民生等十方面政府工作任务。
+国务院总理代表国务院向全国人民代表大会作《政府工作报告》，请予审议，并请全国政协委员提出意见。报告回顾2023年工作，提出2024年经济社会发展总体要求、主要预期目标和政府工作任务。2023年，面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务，全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元、增长5.2%，城镇新增就业1244万人，粮食产量1.39万亿斤再创历史新高。2024年是中华人民共和国成立75周年、实现“十四五”规划目标任务的关键一年，报告坚持稳中求进工作总基调，提出国内生产总值增长5%左右等主要预期目标，部署大力推进现代化产业体系建设、加快发展新质生产力等十个方面政府工作任务，基调积极进取、务实为民。
 # 核心政策
-## 核心政策
-### 2024年经济社会发展总体要求
-- **总体要求**：坚持`稳中求进工作总基调`，完整、准确、全面贯彻新发展理念，加快构建新发展格局，着力推动高质量发展，全面深化改革开放，推动高水平科技自立自强，加大宏观调控力度
-- **统筹关系**：统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全
-- **政策基调**：坚持`稳中求进、以进促稳、先立后破`，多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施
-- **宏观政策取向一致性**：把非经济性政策纳入宏观政策取向一致性评估，确保同向发力、形成合力；涉企政策要注重与市场沟通，回应企业关切，营造稳定、透明、可预期的政策环境
-### 2024年主要预期目标
-- **经济增长**：国内生产总值增长**5%左右**
-- **就业**：城镇新增就业**1120万人以上**，城镇调查失业率**5.5%左右**
-- **物价**：居民消费价格涨幅**3%左右**
-- **居民收入**：居民收入增长和经济增长同步
-- **国际收支**：国际收支保持基本平衡
-- **粮食产量**：粮食产量**1.3万亿斤以上**
-- **能耗**：单位国内生产总值能耗降低**2.5%左右**
-- **生态环境**：生态环境质量持续改善
-### 财政政策
-- **总体取向**：积极的财政政策要`适度加力、提质增效`
-- **赤字率**：赤字率拟按**3%**安排，赤字规模**4.06万亿元**
-- **支出规模**：一般公共预算支出规模**28.5万亿元**
-- **地方政府专项债券**：拟安排**3.9万亿元**
-- **超长期特别国债**：为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，连续几年发行超长期特别国债，专项用于`国家重大战略实施和重点领域安全能力建设`，今年先发行**10000亿元**
-- **支出结构**：大力优化支出结构，强化国家重大战略任务和基本民生财力保障；中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜；省级财政推动财力下沉，兜牢基层`三保`底线
-- **过紧日子要求**：各级政府要习惯过紧日子，切实把财政资金用在刀刃上、用出实效
-### 货币政策
-- **总体取向**：稳健的货币政策要`灵活适度、精准有效`
-- **流动性**：保持流动性合理充裕，社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配
-- **融资成本**：促进社会综合融资成本稳中有降
-- **资本市场**：增强资本市场内在稳定性
-- **汇率**：保持人民币汇率在合理均衡水平上基本稳定
-### 产业与创新政策
-- **现代化产业体系**：大力推进现代化产业体系建设，加快发展`新质生产力`
-- **产业链优化升级**：实施`制造业重点产业链高质量发展行动`，着力补齐短板、拉长长板、锻造新板，推动传统产业高端化、智能化、绿色化转型
-- **中小企业**：促进中小企业`专精特新`发展，加强标准引领和质量支撑，打造更多有影响力的"中国制造"品牌
-- **战略性新兴产业**：促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资
-- **数字经济**：制定支持数字经济高质量发展政策，开展`人工智能+`行动，实施`制造业数字化转型行动`，大力推动数据开发开放和流通使用
-- **科教兴国**：深入实施`科教兴国战略`，制定实施`教育强国建设规划纲要`，开展`基础教育扩优提质行动`
-- **科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发，强化企业科技创新主体地位
-- **人才政策**：实施更加积极、更加开放、更加有效的人才政策，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系
-### 内需与开放政策
-- **消费**：从增加收入、优化供给、减少限制性措施等方面综合施策，实施`数字消费、绿色消费、健康消费促进政策`，鼓励和推动消费品以旧换新，推动养老、育幼、家政等服务扩容提质
-- **投资**：发挥政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施`十四五规划重大工程项目`，着力稳定扩大民间投资
-- **外贸**：推动外贸`稳规模、优结构`，支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，出台服务贸易、数字贸易创新发展政策
-- **外资**：**全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，深入实施`自贸试验区提升战略`
-- **一带一路**：推动高质量共建`一带一路`走深走实，抓好`支持高质量共建一带一路八项行动`落实落地，稳步推进重大项目合作，实施一批"小而美"民生项目，加快建设西部陆海新通道
-### 改革与风险防控政策
-- **经营主体活力**：不断完善落实`两个毫不动摇`的体制机制，深入实施`国有企业改革深化提升行动`，全面落实促进民营经济发展壮大的意见及配套举措，实施`降低物流成本行动`，健全防范化解拖欠企业账款长效机制
-- **全国统一大市场**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题
-- **财税金融改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革
-- **房地产**：优化房地产政策，促进房地产市场平稳健康发展，加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求
-- **地方债务**：统筹好地方债务风险化解和稳定发展，进一步落实`一揽子化债方案`，建立同高质量发展相适应的政府债务管理机制
-- **中小金融机构**：稳妥推进一些地方的中小金融机构风险处置
-- **粮食安全**：全方位夯实粮食安全根基，稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平
-- **能源资源安全**：强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定
-### 三农与区域协调政策
-- **乡村振兴**：学习运用`千村示范、万村整治工程`经验，推动乡村全面振兴
-- **脱贫攻坚成果巩固**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度
-- **土地承包**：**启动第二轮土地承包到期后再延长30年整省试点**
-- **新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善`人地钱挂钩`政策，推动未落户常住人口平等享受城镇基本公共服务
-- **区域战略**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展
-### 生态文明政策
-- **总体路径**：深入践行`绿水青山就是金山银山`理念，协同推进降碳、减污、扩绿、增长
-- **污染防治**：深入实施`空气质量持续改善行动计划`，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好`三北工程三大标志性战役`
-- **绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区
-- **碳达峰碳中和**：积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系
-### 民生保障政策
-- **就业**：突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过**1170万人**，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作
-- **居民收入**：多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收
-- **医疗卫生**：居民医保人均财政补助标准提高**30元**，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新
-- **社会保障**：城乡居民基础养老金月最低标准提高**20元**，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担
-- **社会救助**：健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢
-- **文化建设**：创新实施`文化惠民工程`，大力发展文化产业，推动全民健身活动广泛开展
-- **社会治理**：贯彻总体国家安全观，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生，坚持和发展新时代`枫桥经验`，推进矛盾纠纷预防化解，推动信访工作法治化
+## 2024年经济社会发展总体要求与政策取向
+- **总体要求**：坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，加快构建新发展格局，着力推动高质量发展，全面深化改革开放，推动高水平科技自立自强，加大宏观调控力度，统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全。
+- **政策基调**：坚持稳中求进、以进促稳、先立后破，多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施；在转方式、调结构、提质量、增效益上积极进取，强化宏观政策逆周期和跨周期调节。
+- **形势研判**：今年我国发展面临的环境仍是战略机遇和风险挑战并存，**有利条件强于不利因素**；实现今年预期目标并非易事，需要政策聚焦发力、工作加倍努力、各方面齐心协力。
+## 2024年主要预期目标
+- **经济增长**：国内生产总值增长**5%左右**。
+- **就业**：城镇新增就业**1120万人**，城镇调查失业率**5.5%左右**。
+- **物价**：居民消费价格涨幅**3%左右**。
+- **收入**：居民收入增长和经济增长同步。
+- **国际收支**：国际收支保持基本平衡。
+- **粮食安全**：粮食产量**1.3万亿斤以上**。
+- **能耗**：单位国内生产总值能耗降低**2.5%左右**。
+- **生态**：生态环境质量持续改善。
+## 财政政策
+- **赤字率**：拟按**3%**安排，赤字规模**4.06万亿元**。
+- **支出规模**：一般公共预算支出规模**28.5万亿元**。
+- **地方政府专项债券**：拟安排**3.9万亿元**。
+- **超长期特别国债**：为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，**今年先发行10000亿元**。
+- **支出结构优化**：大力优化支出结构，强化国家重大战略任务和基本民生财力保障；中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜；省级财政要推动财力下沉，兜牢基层`三保`底线。
+- **过紧日子**：各级政府要习惯过紧日子，切实把财政资金用在刀刃上、用出实效。
+## 货币政策
+- **总体取向**：稳健的货币政策要灵活适度、精准有效，保持流动性合理充裕。
+- **融资与货币供应**：社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配。
+- **融资成本**：促进社会综合融资成本稳中有降。
+- **资本市场与汇率**：增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。
+## 宏观政策取向一致性
+- **政策协调配合**：围绕发展大局加强政策协调配合，把非经济性政策纳入宏观政策取向一致性评估，确保同向发力、形成合力。
+- **政策制定程序**：各地区各部门制定政策要认真听取和吸纳各方面意见，涉企政策要注重与市场沟通、回应企业关切，营造稳定、透明、可预期的政策环境。
+## 2024年政府工作任务总体部署
+- **工作总纲**：深入贯彻习近平经济思想，集中精力推动高质量发展，强化系统观念，把握和处理好重大关系，以更大的决心和力度深化改革开放，持续激发和增强社会活力。
+- **任务框架**：党中央对今年工作作出全面部署，涵盖大力推进现代化产业体系建设、深入实施科教兴国战略、着力扩大国内需求、坚定不移深化改革、扩大高水平对外开放、更好统筹发展和安全、坚持不懈抓好三农工作、推动城乡融合和区域协调发展、加强生态文明建设、切实保障和改善民生等十个方面。
+## 现代化产业体系建设
+- **产业链供应链优化升级**：保持工业经济平稳运行，实施`制造业重点产业链高质量发展`行动，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的`中国制造`品牌。
+- **战略性新兴产业**：促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
+- **数字经济**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展`人工智能+`行动，实施`制造业数字化转型`行动，大力推动数据开发开放和流通使用。
+## 科教兴国战略
+- **高质量教育体系**：全面贯彻党的教育方针，制定实施`教育强国建设规划纲要`，落实立德树人根本任务，开展`基础教育扩优提质`行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
+- **高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发；强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作。
+- **人才政策**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
+## 扩大国内需求
+- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
+- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施`十四五`规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
+## 深化改革
+- **激发各类经营主体活力**：不断完善落实`两个毫不动摇`的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施`国有企业改革深化提升`行动，全面落实促进民营经济发展壮大的意见及配套举措，实施`降低物流成本`行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投。
+- **全国统一大市场**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
+- **财税金融改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
+## 扩大高水平对外开放
+- **外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
+- **加大吸引外资力度**：**全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施`自贸试验区提升`战略，打造对外开放新高地。
+- **共建一带一路**：推动高质量共建`一带一路`走深走实，抓好支持高质量共建`一带一路`八项行动落实落地，稳步推进重大项目合作，实施一批`小而美`民生项目，加快建设西部陆海新通道。
+- **多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
+## 统筹发展和安全
+- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案；稳妥推进一些地方的中小金融机构风险处置。
+- **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
+- **重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
+## 三农工作与乡村全面振兴
+- **粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平；各地区都要扛起保障国家粮食安全责任。
+- **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
+- **农村改革与发展**：启动**第二轮土地承包到期后再延长30年整省试点**，促进农民增收，壮大乡村富民产业；深入实施`乡村建设`行动，持续改善农村人居环境，建设宜居宜业和美乡村。
+## 城乡融合与区域协调发展
+- **新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务；新型城镇化要处处体现以人为本。
+- **区域协调发展**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
+## 生态文明建设
+- **生态环境综合治理**：深入践行`绿水青山就是金山银山`理念，协同推进降碳、减污、扩绿、增长；深入实施`空气质量持续改善行动计划`，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好`三北`工程三大标志性战役，完善生态产品价值实现机制。
+- **绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
+- **碳达峰碳中和**：积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
+## 保障和改善民生
+- **稳就业促增收**：突出就业优先导向，加大促就业专项政策力度；**预计今年高校毕业生超过1170万人**，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
+- **医疗卫生服务**：居民医保人均财政补助标准**提高30元**；深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展`健康中国`行动和爱国卫生运动。
+- **社会保障**：城乡居民基础养老金月最低标准**提高20元**，继续提高退休人员基本养老金；加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢。
+- **文化体育事业**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施`文化惠民工程`，大力发展文化产业，推动全民健身活动广泛开展。
+- **国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代`枫桥经验`，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
 # 重点工作
-## 现代化产业体系建设
-- **推动产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板，推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌
-- **促进战略性新兴产业融合集群发展**：巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资
-- **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展“人工智能+”行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用
-## 科教兴国战略
-- **加强高质量教育体系建设**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务，开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科
-- **加快推动高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发，强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作，营造具有全球竞争力的开放创新生态
-- **全方位培养用好人才**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系
-## 扩大国内需求
-- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策，稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费，推动养老、育幼、家政等服务扩容提质，优化消费环境
-- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施“十四五”规划重大工程项目，着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为
-## 深化改革
-- **激发各类经营主体活力**：不断完善落实“两个毫不动摇”的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境，深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投
-- **加快全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序
-- **推进财税、金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革
-## 扩大高水平对外开放
-- **推动外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策
-- **加大吸引外资力度**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施自贸试验区提升战略，打造对外开放新高地
-- **推动高质量共建“一带一路”走深走实**：抓好支持高质量共建“一带一路”八项行动落实落地，稳步推进重大项目合作，实施一批“小而美”民生项目，加快建设西部陆海新通道
-- **深化多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济
-## 统筹发展和安全
-- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任，优化房地产政策，促进房地产市场平稳健康发展，统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置
-- **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求，建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力
-- **加强重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定
-## 乡村全面振兴
-- **加强粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平，各地区都要扛起保障国家粮食安全责任
-&gt; 我们这样一个人口大国，必须始终把饭碗牢牢端在自己手上。
-- **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续
-- **稳步推进农村改革发展**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业，深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村
-## 城乡融合和区域协调发展
-- **积极推进新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务
-- **提高区域协调发展水平**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划
-## 生态文明建设
-- **推动生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好“三北”工程三大标志性战役，完善生态产品价值实现机制
-- **大力发展绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区
-- **积极稳妥推进碳达峰碳中和**：扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求
-## 保障和改善民生
-- **多措并举稳就业促增收**：突出就业优先导向，加大促就业专项政策力度，预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作，多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收
-- **提高医疗卫生服务能力**：居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展健康中国行动和爱国卫生运动
-- **加强社会保障**：城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担，健全分层分类的社会救助体系
-- **丰富人民群众精神文化生活**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展
-- **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生，完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代“枫桥经验”，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动
-## 政府自身建设
-- **深入推进依法行政**：严格遵守宪法法律，自觉接受同级人大及其常委会的监督，自觉接受人民政协的民主监督，自觉接受社会和舆论监督，加强审计监督，坚持科学民主依法决策，支持工会、共青团、妇联等群团组织更好发挥作用
-- **纵深推进党风廉政建设和反腐败斗争**：发扬自我革命精神，政府工作人员要遵守法纪、廉洁修身、勤勉尽责，干干净净为人民服务
-- **全面提高行政效率**：深入推进政府职能转变，不断提高执行力和公信力，在抓落实上切实做到不折不扣、雷厉风行、求真务实、敢作善为，坚决纠正形式主义、官僚主义，持续为基层和企业减负
-## 民族、宗教、侨务与国防外交
-- **促进民族团结与宗教和谐**：以铸牢中华民族共同体意识为主线，促进各民族广泛交往、交流、交融，坚持党的宗教工作基本方针，深入推进我国宗教中国化，加强和改进侨务工作
-- **加强国防和军队建设**：深入贯彻习近平强军思想，贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全面深入贯彻军委主席负责制，打好实现建军一百年奋斗目标攻坚战，全面加强练兵备战，抓好军队建设“十四五”规划执行，加快实施国防发展重大工程，各级政府要大力支持国防和军队建设
-- **港澳台工作**：继续全面准确、坚定不移贯彻“一国两制”、“港人治港”、“澳人治澳”、高度自治的方针，坚持依法治港治澳，落实爱国者治港、爱国者治澳原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局；坚持贯彻新时代党解决台湾问题的总体方略，坚持一个中国原则和“九二共识”，坚决反对“台独”分裂和外来干涉，推动两岸关系和平发展，深化两岸融合发展
-- **大国外交**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体</t>
+## 大力推进现代化产业体系建设，加快发展新质生产力
+- **推动产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌。
+- **促进战略性新兴产业融合集群发展**：巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
+- **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展“人工智能+”行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
+## 深入实施科教兴国战略，强化高质量发展的基础支撑
+- **加强高质量教育体系建设**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务，开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
+- **加快推动高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发；强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作，营造具有全球竞争力的开放创新生态。
+- **全方位培养用好人才**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
+## 着力扩大国内需求，推动经济实现良性循环
+- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
+- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施“十四五”规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
+## 坚定不移深化改革，增强发展内生动力
+- **激发各类经营主体活力**：不断完善落实“两个毫不动摇”的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投。
+- **加快全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
+- **推进财税、金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
+## 扩大高水平对外开放，促进互利共赢
+- **推动外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
+- **加大吸引外资力度**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施自贸试验区提升战略，打造对外开放新高地。
+- **推动高质量共建“一带一路”走深走实**：抓好支持高质量共建“一带一路”八项行动落实落地，稳步推进重大项目合作，实施一批“小而美”民生项目，加快建设西部陆海新通道。
+- **深化多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
+## 更好统筹发展和安全，有效防范化解重点领域风险
+- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案；稳妥推进一些地方的中小金融机构风险处置。
+- **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
+- **加强重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
+## 坚持不懈抓好“三农”工作，扎实推进乡村全面振兴
+- **加强粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平。
+&gt; 各地区都要扛起保障国家粮食安全责任。我们这样一个人口大国，必须始终把饭碗牢牢端在自己手上。
+- **毫不放松巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
+- **稳步推进农村改革发展**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业；深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
+## 推动城乡融合和区域协调发展，大力优化经济布局
+- **积极推进新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
+- **提高区域协调发展水平**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
+## 加强生态文明建设，推进绿色低碳发展
+- **推动生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好“三北”工程三大标志性战役，完善生态产品价值实现机制。
+- **大力发展绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
+- **积极稳妥推进碳达峰碳中和**：扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
+## 切实保障和改善民生，加强和创新社会治理
+- **多措并举稳就业促增收**：突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
+- **提高医疗卫生服务能力**：居民医保人均财政补助标准提高30元；深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展健康中国行动和爱国卫生运动。
+- **加强社会保障**：城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金；加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢。
+- **丰富人民群众精神文化生活**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。
+- **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代“枫桥经验”，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>47.7</v>
+        <v>58.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9903/8469</t>
+          <t>9903/8888</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11247,7 @@
       <c r="C31" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-杭州医学院检验医学院、生物工程学院通过B站、微博、抖音等平台举办专场直播，面向考生及家长介绍医学技术专业硕士点招生情况。直播由检验医学院、生物工程学院党委书记、副院长宋宝峰副教授主讲，围绕学位点基本情况、学科建设与优势、研究方向、师资队伍、培养与就业、2026年招考计划及复试安排等主题展开，并现场解答考生关于就业前景、初试科目、跨专业报考等疑问。整体基调为积极推介，强调该学位点学科实力与就业竞争力，鼓励考生报考。
+杭州医学院检验医学院、生物工程学院通过B站、微博、抖音等平台开展专场直播，由学院党委书记、副院长宋宝峰副教授面向考生及家长介绍医学技术专业硕士点的招生情况与培养特色。该学位点于2024年获批，由检验医学院、生物工程学院（合署办公）牵头，联合医学影像学院、康复学院、信息工程学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向。直播围绕学位点基本情况、学科建设与优势、研究方向、师资队伍、培养与就业、2026年招考计划及复试安排等展开，并现场解答考生关于就业前景、初试科目、跨专业报考等疑问。整体基调为积极推介，强调学科实力与就业竞争力，欢迎考生报考。
 # 核心信息与数据
 ## 学位点基本情况
 - **学位点获批**：医学技术专业硕士点于2024年获批，为新增学位点。
@@ -11268,81 +11256,81 @@
 ## 2025年招生情况
 - **录取人数**：2025年录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
 ## 学科建设与科研平台
-- **学科层次**：2023年获批浙江省医学技术省一流学科B类。
-- **科研项目**：近五年获国家级基金项目19项、省鉴定领先项目1项。
-- **科研经费**：纵向科研经费1300万元，横向合作课题经费2200多万元。
-- **科研成果**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
-- **教学建设**：建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
-- **省级平台**：建有省生物标志物与器官诊断转化重点实验室、检验诊断关键技术研究室、康复模块和机器人国际联合实验室、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、省神经系统疾病数字化装备研发重点实验室等省级平台。
+- **学科层次**：医学技术于2023年获批浙江省一流学科B类。
+- **科研项目与经费**：近五年获国家级基金项目19项、省鉴定领先项目1项；纵向科研经费1300万元，横向合作课题经费2200多万元。
+- **科研获奖**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
+- **课程与专业建设**：建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
+- **省级科研平台**：建有省生物标志物与器官诊断转化重点实验室（2024年获批）、检验诊断关键技术研究室（2022年）、康复模块和机器人国际联合实验室（2023年）、省实验室和安全培训基地、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、浙江省神经系统疾病数字化装备研发重点实验室（2024年）等。
 ## 学科优势
-- **体外诊断领域**：优势显著，疫情期间与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册。
-- **医学影像技术**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优质方向，拥有国家级本科专业建设点、省医学重点学科、省临床放射质控中心、国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地等平台。
+- **体外诊断领域**：疫情期间与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册；为中华医学会检验医学分会教育学组组长单位、卫生高新技术公司实体开发基地。
+- **医学影像技术方向**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向，建有国家级本科专业建设点、省医学重点学科、省临床放射质控中心、国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地等平台。
 - **康复治疗方向**：依托省人民医院康复医学科，为省内综合医院中建科最早、人才最齐、技术最先进、设备最先进、社会效益最佳的康复医学科之一。
-- **智能医学工程**：聚焦阿尔茨海默病智能预警生物标志物（数字生物标志物），居国际领跑水平，为浙江省中医药重点学科、老年助浴疾病数字器械医疗器械浙江省中心、智能医学前沿交叉学院。
+- **智能医学工程方向**：聚焦阿尔茨海默病智能预警数字生物标志物，居国际领跑水平；为浙江省中医药重点学科、老年助浴疾病数字器械医疗器械浙江省中心、智能医学前沿交叉学院。
 ## 主要研究方向
-- **医学检验技术（负责人吕建新教授）**：聚焦重大疾病新型生物标志物筛选及机制研究、新发突发传染病新型生物标志物筛选及致病机制研究、重大疾病体外诊断检测技术研究、新型药物系统体内治疗易复发难治愈疾病研究、神经免疫与再生研究五个方向；团队在线粒体氧化磷酸化功能改变与线粒体相关疾病、新冠病毒快速检测试剂等方面取得突破，发表高水平论文百余篇。
-- **卫生检验检疫（负责人金大志教授）**：聚焦新发突发传染病病原体检测检验新技术方法开发（含艰难梭菌致病机制、耐药机制、基因组进化及小分子药物开发）和卫生检验技术研究；获省科技进步二等奖、三等奖各1项，省医药卫生科技进步一等奖1项、二等奖2项、三等奖1项，发表中科院一二区论文85篇，主编专业教材12部、主审7部。
-- **医学影像技术（负责人徐秀芳教授）**：聚焦多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位研究四个方向；获国家自然科学基金3项、省部级项目20多项，获全国优秀教材二等奖1项。
-- **康复治疗（负责人倪湘明教授）**：聚焦康复技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病机制及临床研究五个方向；团队获国家级课题23项、省级课题23项，省科技进步三等奖2项、省医药卫生科技进步奖二等奖2项，国家发明专利和实用新型专利77项，主编专业书籍、主审教材8部、参编书籍40多部。
-- **智能医学工程（负责人李海教授）**：聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病（阿尔茨海默病、帕金森病、抑郁症、自闭症等）智能诊断及数字方向五个方面；主持参与国家级项目3项、省部级重点研发计划及200万以上重大设计项目，与中国人民解放军总院、浙一医院、日本文化研究所等单位开展合作；与浙大联合研制的阿尔茨海默病数字预警仪已申报二类医疗器械。
+- **医学检验技术方向**：负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制、新发突发传染病新型生物标志物筛选及致病机制、重大疾病体外诊断检测技术、新型药物系统治疗难治性疾病、神经免疫与再生五个方向；团队承担多项国家级和省部级项目，在线粒体氧化磷酸化功能改变与线粒体相关疾病、新冠病毒快速检测试剂方面取得突破，发表高水平论文百余篇。
+- **卫生检验检疫方向**：负责人金大志研究员，聚焦新发突发传染病病原体检测检验新技术开发（艰难梭菌致病机制、耐药机制、基因组进化及小分子药物开发）和卫生检验技术研究；获省科技进步二等奖、三等奖各1项，省医药卫生科技进步一等奖1项、二等奖2项、三等奖1项，发表中科院一二区论文85篇，主编专业教材12部、主审7部。
+- **医学影像技术方向**：负责人徐秀芳教授，研究多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位四个方向；主持国家自然科学基金3项、省部级项目20多项，获全国优秀教材二等奖1项。
+- **康复治疗方向**：负责人倪湘明教授（附属人民医院），研究康复技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病五个方向；团队获国家级课题23项、省级课题23项，省科技进步三等奖2项、省医药卫生科技进步二等奖2项，国家发明专利和实用新型专利77项，主编专业书籍、主审教材8部、参编书籍40多部。
+- **智能医学工程方向**：负责人李海教授，聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病（阿尔茨海默病、帕金森病、抑郁症、自闭症等）智能诊断五个方向；主持参与国家级项目3项、省部级重点研发计划及200万元以上重大设计项目，与中国人民解放军总医院、浙一医院、日本文化研究所等单位开展合作；与浙大联合研制的阿尔茨海默病数字预警仪已申报二类医疗器械。
 ## 师资队伍与领军人物
-- **师资规模**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，其中正高35人、博士46人。
+- **师资总体情况**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，其中正高35人、博士46人；专业背景涵盖临床检验诊断学、医学检验技术、影像技术、康复治疗学、智能医学工程、生化分子、免疫生物技术、微生物学、细胞生物学等。
 - **人才称号**：教育部医学技术类专业教学指导委员会委员1人，省万人创新人才2人次，浙江省151人才5人，省杰青1人，省高层次创新人才2人，省领军型创新创业团队1个。
-- **吕建新教授**：学位点负责人，博士，国家百千万人才工程人选、国家行业企业专家、省万人计划领军人才，教育部医学技术类专业教学指导委员会委员、国家自然基金会医学技术检验学科专家组长、中华医学会检验学会教育学组组长；主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表高水平论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项。
-- **徐秀芳教授**：博士，浙江省151人才第三层次人才、省高校中青年学科带头人，现任研究生院院长兼医学影像学院院长，国家一流本科专业建设点医学影像技术专业负责人，教育部教指委相关医学分会委员、中华医学会影像技术分会影像技术专委会委员；近三年以通讯作者或第一作者在国际知名期刊发表多篇高水平论文。
+- **吕建新教授**：学位点负责人，博士，国家百千万人才工程入选者、国家行业专家、省万人计划领军人才；教育部医学技术类专业教学指导委员会委员、国家自然科学基金医学技术检验学科专家组组长、中华医学会检验学会教育学组组长；主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表高水平论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项。
+- **徐秀芳教授**：博士，浙江省151人才第三层次、省高校中青年学科带头人，现任研究生院院长兼医学影像学院院长，国家一流本科专业建设点（医学影像技术）负责人，教育部教指委相关医学分会委员、中华医学会影像技术分会委员；近三年以通讯作者或第一作者发表多篇高水平论文。
 - **叶祥明教授**：省人民医院主任医师、二级教授、博导、博士后导师，省康复中心主任、康复学院院长、省卫生领军人才、国家区域医疗中心浙江省重点培育专科康复医学学科带头人、数字化康复装备省部研究中心常务副主任；主持国家级课题3项、省重大课题2项，发表SCI论文98篇。
-- **金大志研究员**：博士、硕导，美国华盛顿大学博士后、美国MSCC访问学者，省创新人才、卫生创新人才、省首届优秀医疗机器人才，现任检验医学院学术院长、省生物标志物与器官诊断转化重点实验室主任、中国医师协会临床微生物分会常务委员；主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划、省自然基金重点项目、省部共建重大项目共25项，发表SCI论文50多篇，参编专著6部，获省科技进步二等奖、三等奖各1项及美国微生物学年会重要奖项。
-- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士、早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长、智能医学工程学科负责人、浙江省中医药重点学科带头人、智慧健康装备省工程研究中心主任；参与研制全生命周期中医治疗及康复医疗体系设备3台/套。
+- **金大志研究员**：博士、硕导，美国华盛顿大学博士后、美国MSCC访问学者，省创新人才、省卫生创新人才、省首届优秀医疗机器人才，现任检验医学院学术院长、省生物标志物与器官诊断转化重点实验室主任、中国医师协会临床微生物分会常务委员；主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划、省自然基金重点项目、省部共建重大项目共25项，发表SCI论文50多篇，参编专著6部，获省科技进步二等奖、三等奖各1项及美国微生物学年会重要奖项。
+- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士、早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长、智能医学工程学科负责人、浙江省中医药重点学科带头人，智慧健康装备领域专家；参与研制全生命周期中医治疗及康复医疗体系设备3台（套）。
 ## 硕士培养与毕业去向
 - **培养目标**：面向健康中国发展需要，紧密服务区域行业产业发展，围绕国际学术前沿、国际重大需求和转化研究，培养熟练掌握医学技术领域专业知识技能、具有良好创新实践能力的高层次应用型人才。
-- **培养方式**：采用教学、专业实践与学位论文相结合的方式。
-- **学制**：全日制专业学位学制三年，最长不超过五年。
-- **学分要求**：毕业前学业课程不少于24学分，其中专业必修课≥12学分（分方向），专业选修课≥6学分（含智慧医疗、中医康复治疗学、生物信息学等）。
-- **培养环节**：第二学期开题，第三、四学期（研二）完成过程性考核，第二学期进行学位论文答辩。
-- **就业方向（医院）**：检验方向可进入检验科、输血科、病理科；影像技术方向可进入放射科、超声科；康复治疗方向可进入康复医学科、骨科、神经科、运动医学科；卫检方向可进入疾病预防控制中心（CDC）参与传染病防控、慢性病防治等公共卫生工作。
-- **就业方向（企业）**：医药企业与生物技术公司（研发、生产、市场销售、质量管理与法规合规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）。
-- **就业方向（其他）**：药监局、卫健委、海关（医疗器械监管、卫生政策制定、口岸卫生检疫），高校、研究所继续深造（读博或从事研究）。
+- **培养方式与学制**：采用教学、专业实践与学位论文相结合方式；全日制专业学位学制三年，最长不超过五年。
+- **学分要求**：实行学分制，毕业前学业课程不少于24学分，其中专业必修课≥12学分（分方向），专业选修课≥6学分（可选智慧医疗、中医康复治疗学、生物信息学等）。
+- **培养环节**：第二学期开题，第三、四学期（研二）完成过程性考核，研二第二学期进行学位论文答辩。
+- **就业方向**：医院相关科室（检验方向可进检验科、输血科、病理科；影像方向可进放射科、超声科；康复方向可进康复医学科、骨科、神经科、运动医学科）、疾控中心（CDC，参与传染病防控、慢性病防治等公共卫生工作）、医药企业与生物技术公司（研发、生产、市场销售、质量管理与法规合规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）、药监局/卫健委/海关（医疗器械监管、卫生政策制定、口岸卫生检疫）、高校及研究所（读博深造或从事研究）。
+- **就业现状**：2025年开始招生，目前尚无毕业生。
 ## 2026年招考计划
-- **计划招生**：2026年计划招生34人，实际以教育部正式下达人数为准。
-- **初试科目**：思想政治理论、英语为统考科目，专业课按方向自主命题——检验考检验综合、影像技术考医学影像技术综合、康复治疗考康复治疗综合、智能医学工程考智能医学工程综合。
-- **专业课内容**：检验技术考分子生物学检验、生物化学检验、微生物学检验。
-- **考试大纲**：专业综合课程为学校自命题，实践分值300分、考试时长180分钟；检验综合占比为卫生生物学检验40%、生物化学检验30%、微生物学检验30%。
-- **复试安排**：初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%；目前以线下复试为主。
-- **信息渠道**：考试大纲、参考书目等以杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）及研究生教育微信公众号公布为准。
+- **计划招生**：2026年计划招生34人，仅供参考，以教育部正式下达人数为准。
+- **初试科目**：共三门，思想政治理论、英语为统考科目，专业课按方向自主命题：检验方向考检验综合、影像方向考医学影像技术综合、康复方向考康复治疗综合、智能医学工程方向考智能医学工程综合。
+- **检验综合考试内容**：分子生物学检验占40%、生物化学检验占30%、微生物学检验占30%。
+- **考试形式**：专业课满分300分，考试时长180分钟，考试大纲含考试内容、形式、试卷结构、知识点及参考书目，以杭州医学院研究生招生网公布为准。
+- **复试安排**：目前以线下为主，初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%，实行导师学生双向选择制。
+- **信息渠道**：杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）、杭州医学院研究生教育微信公众号。
 # 各方立场与诉求
-- **考生（经主持人转述）**：关注当前经济形势下医学技术专业研究生毕业后的就业前景，询问就业出口是否广泛、研究生学历是否具有竞争力。
-- **宋宝峰（回应就业前景）**：强调国家就业优先政策，学校将就业工作放在重要位置；指出本专业就业面广，毕业生可进入三甲医院、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等单位，也可继续读博深造；认为杭州高水平三甲医院和企业对研究生及以上学位者具有较强需求，研究生学历具备核心竞争力，考生不必过度担心和焦虑。
-- **考生（经主持人转述）**：询问硕士研究生入学考试初试科目有哪些，以便利用暑期时间备考。
-- **宋宝峰（回应初试科目）**：说明医学技术初试共三门，其中思想政治理论、英语为统考，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；英语难度介于四级和六级之间，建议以研究生考试英语真题为参照；思政需与时俱进学习备考；专业课备考可关注杭州医学院研究生招生网及研究生教育微信公众号获取考试大纲、参考教材等信息。
-- **考生（经主持人转述）**：关注跨专业报考问题，担心非本专业考生备考节奏跟不上。
-- **宋宝峰（回应跨专业报考）**：明确表示医学技术专业鼓励跨学科跨专业报考，允许本科非本专业的考生（如从事检验方向）跨专业自主报考，并认为跨专业考生被录取的概率会大大提高。
-- **考生（经主持人转述）**：关注学校地理位置与交通条件，以及研究生能否参加学科竞赛。
-- **宋宝峰（回应交通与竞赛）**：介绍学校有三个校区（滨江校区等），主体位于主城区黄路校区，交通便利；表示学校重视竞赛，研究生在竞赛中取得良好成绩，设有资源提升改善、专门选手讲座与培训等支持体系，通过以赛促学、以赛促教、以赛促改提升教学质量与人才培养水平。
+- **主持人**：代表后台考生提出就业前景关切，询问在当前经济形势下医学技术专业研究生毕业后的就业前景。
+- **宋宝峰**：回应称国家坚持就业优先，该专业就业面宽广、有竞争力，毕业生可继续深造读博，也可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等单位，研究生学历在杭州高水平三甲医院和企业中具有核心竞争力，呼吁考生不必过度担心和焦虑。
+- **主持人**：代考生询问硕士研究生入学考试初试科目有哪些，以便利用暑期备考。
+- **宋宝峰**：回应称初试共三门，思想政治理论和英语为统考，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合），并建议考生暑期重点备考，英语难度介于四级和六级之间，可参考研究生考试英语真题，同时关注杭州医学院研究生招生网和研究生教育微信公众号获取考试大纲与参考教材。
+- **主持人**：代考生询问跨专业报考的可能性，称有考生担心节奏快不起来。
+- **宋宝峰**：回应称医学技术专业鼓励跨学科跨专业报考，允许非本专业考生跨专业报考医学技术学位点，如从事检验方向可以跨专业自主报考，被录取概率会大大提高。
+- **主持人**：代考生询问学校交通条件和能否参加学科竞赛。
+- **宋宝峰**：回应称学校有三个校区，主校区在黄龙校区，位于主城区，交通便利；学校重视学科竞赛，研究生在竞赛中取得好成绩，有专门的选手讲座和培训，通过以赛促学、以赛促教、以赛促改提高教学质量和人才培养水平。
 # 达成共识
-- **2026年计划招生人数**：初试计划招生34人，实际招生人数以教育部2026年正式下达为准，**宋宝峰明确表示该数字仅供参考**。
-- **初试科目口径**：思想政治理论、英语为统考科目，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）。
-- **复试占比与内容**：复试占比为初试60%、复试40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%。
-- **跨专业报考**：**允许并鼓励非本专业考生跨专业报考医学技术专业硕士点**，宋宝峰表示「允许啊这个本科的就是非该专业的……可以跨专业自主报考的啊，这个大家放心」。
-- **就业前景判断**：宋宝峰确认就业面广，研究生学历在杭州高水平三甲医院及企业中具有核心竞争力，**对毕业生就业前景表示有信心**。
+- **学位点定位**：医学技术专业硕士点为2024年获批的新学位点，由检验医学院、生物工程学院（合署办公）牵头，医学影像学院、康复学院、信息工程学院共建，聚焦检验技术（医检、卫检）、医学影像技术、康复治疗、智能医学工程四个方向。
+- **2025年招生口径**：2025年录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
+- **2026年计划招生口径**：2026年计划招生34人，宋宝峰明确说明该数字仅供参考，**实际招生人数以教育部2026年正式下达人数为准**。
+- **初试科目口径**：初试共三门，思想政治理论、英语为统考科目，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）。
+- **复试安排口径**：复试目前以线下为主，初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%。
+- **跨专业报考口径**：宋宝峰明确表示**允许非本专业考生跨专业报考医学技术专业**，并称跨专业报考被录取的概率会大大提高。
+- **就业前景口径**：宋宝峰确认就业面宽广，包括深造读博、三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等方向，研究生学历具有核心竞争力。
+- **考试信息发布渠道**：宋宝峰确认考试大纲、参考书目等以杭州医学院研究生招生网及研究生教育微信公众号公布为准。
 # 待协调事项与后续
 ## 待协调事项
-- **2026年实际招生人数**：以教育部正式下达为准，当前计划招生34人仅为参考
-- **复试具体形式和内容**：以学校复试录取办法为基础，目前可参考2025年复试办法；复试形式受条件影响，疫情期间线上、目前以线下为主，存在变化可能
+- **2026年计划招生人数**：目前公布为34人，仅供考生参考，实际招生人数以教育部2026年正式下达人数为准
+- **初试参考书及考试大纲**：以杭州医学院研究生招生网公布为准，直播中仅作初步介绍
+- **复试具体形式与内容**：以学校复试录取办法为基础，目前可参考2025年复试办法
 ## 后续安排与参与方式
 - **直播回看**：本场直播结束后24小时内上传至B站，考生可随时搜索回看
-- **招生信息渠道**：杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）、杭州医学院官网、杭州医学院研究生教育微信公众号
-- **初试备考**：暑期为关键备考期；英语难度介于四级和六级之间，可参考研究生考试英语真题；思想政治理论需与时俱进学习
-- **考试大纲与参考书目**：以杭州医学院研究生招生网公布为准，含考试内容、形式、试卷结构、具体知识点及参考书目
-- **复试安排**：初试占60%、复试占40%；复试含英语能力测试20%、专业能力测试40%、综合能力测试40%，实行导师学生双向选择制，可关注导师风采
-- **跨专业报考**：允许并鼓励非本专业考生跨专业报考医学技术专业硕士点</t>
+- **招生信息渠道**：持续关注杭州医学院官网及杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）
+- **微信公众号**：关注「杭州医学院研究生教育」微信公众号，可查看考试方向、考试大纲及参考教材书籍
+- **报考咨询**：考生可通过B站、微博、抖音弹幕区留言提问，直播中有嘉宾点评答疑
+- **学校地址**：杭州医学院有三个校区，主校区位于主城区黄龙校区，交通便利</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>80.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23026/5633</t>
+          <t>23026/5854</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11886,76 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[失败]HTTP 500 非 JSON 响应：Internal Server Error</t>
+          <t># 课程概况
+本次课程为历史小论文写作专题指导课，由老师主讲、学生参与互动。课程围绕小论文写作的核心要点展开，强调观点必须明确、论证一般写两到三条、结构需清晰（可按时间顺序或国内外等逻辑罗列）、结尾需升华观点，并指出写作前需审题、注意要求中的“小红帽”及形成标准，读材料需抓主要信息再细看关系，建议先写题目再罗列事实。课程依次讲解了自命题类、观点提示类和图表信息类题型的解题方法：自命题类需先审题明确要求，以武汉长江大桥为例说明背景部分需按时间顺序先写对内改革再写对外开放；观点提示类需选择核心观点并明确判断，不能照抄材料观点，需结合丝绸之路、四大发明等具体史实论述；图表信息类需快速看题头、横向纵向信息，注意信息之间的关系变化。课程通过例题分析进行实践指导，学生尝试分析各类题目，老师指出其问题并引导完善论述。
+# 核心知识点梳理
+## 小论文写作基本要求
+- **观点明确**：写作必须亮出个人观点，不能只是“几个方面加个名词”的简单陈述，观点需有凝聚力。
+- **论证条数**：论证一般写**两到三条**，不宜过多；写一条难以支撑论点，太多则显冗长。
+- **结构清晰**：可按时间脉络（如先秦、明清时期）、国内外、内政外交等逻辑罗列，必须让阅卷者清楚看到分了几条。
+- **结尾升华**：最后论述需升华观点，不能简单把观点抄一遍；写作目的是升华观点，需简明有力。
+## 写作步骤与方法
+- **审题**：先阅读题目、慢点审题，注意要求中的“小红帽”及形成标准；如要求用世界史知识，就不能用中国史内容。
+- **读材料**：先大概看材料抓主要信息，再细看材料之间的关系，提取有效信息。
+- **列事实**：建议先写好题目，再罗列要用的史实，避免直接写在答题卡上出错后涂改；罗列的事实须与材料相关，不能乱列。
+- **论述顺序**：背景部分按时间顺序写，如“先写对内改革，再写对外开放”，不能颠倒。
+## 自命题类题型
+- **题型特点**：材料引出话题，需自行提炼观点并展开论述；以武汉长江大桥为例，可写“新中国成立”或“改革开放以来”背景。
+- **解题步骤**：审题看要求→读材料抓主要信息→先写题目→罗列相关史实→进行论述。
+- **易错点**：学生易只看到材料表面写得很好，却未明确自己的观点和背景；如写武汉长江大桥，需交代对内改革、对外开放的时间顺序。
+- **背景写法**：背景部分不能直接当成一个版本说，需按时间顺序展开，如先写对内改革再写对外开放。
+## 观点提示类题型
+- **题型特点**：材料给出若干观点，需选择核心观点并明确判断，如“我认为某观点是正确的/错误的”，不能照抄材料观点。
+- **材料示例**：以1940年抗战时期材料为例，包含四个观点——国民应略知本国历史、了解本国历史可维护国家利益、对本国历史有敬意则不会偏激理解、国民了解历史则国家才能发展。
+- **论述要求**：选择观点后需结合具体史实论证，如写“敬畏祖国意志”可引用丝绸之路、四大发明对欧洲的贡献、中华文化优越性等。
+- **易错点**：不能照抄材料观点，需有自己的表述；需注意材料写作的时代背景（如1940年抗战时期），说明为何此时提出该观点。
+## 图表信息类题型
+- **题型特点**：材料以图表、历史地图、建筑图片等形式呈现，需快速提取关键信息。
+- **解题步骤**：先看图表题头、横向纵向信息→注意信息之间的关系变化→提取有效信息→结合材料关系进行分析论述。
+- **历史地图题**：需在地图上画位置、判断地点，如涉及707年、1900年等时间点；注意地图与材料的对应关系。
+- **建筑类图表**：如展现两三个图线，需分析建筑与政治的关系，从建筑角度论述政治主题。
+- **图表关系题**：如涉及共同体、共同外交安全政策、司法和内部合作等大框架制度，需提取三个信息并分析其关系，再下结论。
+## 例题分析
+- **武汉长江大桥题**：学生分析时未明确观点和背景，老师指出应写新中国成立或改革开放背景，按时间顺序先写对内改革再写对外开放。
+- **观点提示材料题**：学生选择第二条观点（了解本国历史可维护国家利益），结合丝绸之路、四大发明对欧洲影响等史实论述，老师评价“写得还可以”。
+- **历史地图题**：涉及中国历代领导等级变化，学生写“古代人的变化与文学”，老师指出可结合儒家思想、社会状态分析各时期（春秋、东汉、宋明）等级变化原因。
+- **官方答案示例**：梁启超认为中国某时期具有合理性，突出“人人独善其身，人人相善其群”，用中华传统精神论证；唐朝国力强盛但民德较高，结论指向国家强盛、民德高尚与制度改善的关系。
+# 课堂互动与答疑
+**学生**：小论文的论证部分一般写几条比较合适？写太多或太少会有什么问题？
+**教师**：论证一般写两到三条即可。写一条往往无法充分支撑论点，写太多则容易分散、难以深入。每条论证都要与材料相关，不能脱离材料乱罗列事实。
+**学生**：写小论文时，审题环节具体要注意什么？
+**教师**：审题要慢，先看题目要求，注意要求中是否有"小红帽"（即限定条件），以及评分标准。例如题目要求用世界史知识作答，就不能只写中国史内容；若限定了范围，也要严格遵循。审题不清是常见失分点。
+**学生**：观点提示类题目中，如何选择和处理材料给出的观点？
+**教师**：要在材料给出的多个观点中选择一个核心观点，明确表达自己认为该观点正确或错误，不能照抄材料原话。论述时需结合具体史实支撑自己的判断，并在结尾升华观点，不能简单重复开头。
+**学生**：图表信息类题目应该从哪些角度快速提取信息？
+**教师**：先看题头和横向、纵向栏目，抓住关键信息，再注意各信息之间的关系和变化趋势。例如历史地图要关注位置关系，数据表要关注数值变化。提取有效信息后再结合所学知识进行分析论述。
+**学生**：写作时是直接写在答题卡上，还是先打草稿？
+**教师**：建议先在草稿纸上写好题目，再罗列要使用的事实，确认逻辑清晰、与材料相关后再誊写到答题卡上，避免写错或涂改导致卷面混乱。
+# 课后任务与学习建议
+## 课堂练习
+- **武汉长江大桥自命题练习**：考点为自命题类小论文审题与背景运用，需结合新中国成立或改革开放背景，按时间顺序先写对内改革再写对外开放，结论要点是明确观点并罗列与材料相关的事实。
+- **观点提示类材料练习**：考点为选择核心观点并明确判断，材料含四个观点（国民应了解本国历史、敬畏祖国意志、通达历史避免偏激、国家发展需历史认知），结论要点是结合丝绸之路、四大发明等史实论述，不能照抄材料观点。
+- **图表信息类练习**：考点为快速提取图表题头、横向纵向关键信息，注意信息间关系变化，结论要点是以历史地图、建筑与政治关系等为例，提取有效信息后进行分析论述。
+- **历史地图绘制练习**：考点为在地图上标注位置与关系，结论要点是注意地图信息与材料、实践的关系，再形成本文论述。
+## 复习重点
+- **观点明确**：小论文必须亮出明确观点，不能只是几个方面加名词的简单陈述，观点需有凝聚力。
+- **论证结构**：论证一般写两到三条，不宜过多，需按时间脉络（如先秦、明清时期）或国内外、内外等逻辑清晰罗列，让老师看清条理。
+- **结尾升华**：最后论述需升华观点，不能简单重复观点内容，要体现写作目的。
+- **审题要求**：注意题目要求中的"小红帽"及形成标准，如要求用世界史知识时不能搞错范围。
+- **材料阅读**：先大概看材料抓主要信息，再细看信息间关系，罗列事实需与材料相关，不能乱罗列。
+## 学习建议
+- **先写题目再作答**：写作前先把题目写好，再罗列要写的事实，避免直接在答题卡上写导致出错或混乱。
+- **观点提示类选核心观点**：需在多个观点中选择一个核心观点，明确判断其正确或错误，并在论点中详细表述，不能照抄材料。
+- **图表类快速抓关键**：迅速看图表题头、横向纵向信息，注意信息间关系变化，提取有效信息后再分析。
+- **结合史实论述**：论述需结合具体史实支撑观点，如丝绸之路、四大发明对欧洲的贡献等，不能只写空泛结论。</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>12357/3382</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12111,140 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[失败]请求异常：HTTPConnectionPool(host='127.0.0.1', port=8003): Max retries exceeded with url: /api/v1/meeting/minutes (Caused by NewConnectionError("HTTPConnection(host='127.0.0.1', port=8003): Failed to establish a new connection: [Errno 111] Connection refused"))</t>
+          <t># 报告概况
+十四届全国人大三次会议于2025年开幕，出席代表2929人，当日出席2880人、缺席49人，出席人数符合法定人数，会议第一项议程为审议政府工作报告，由国务院总理李强代表国务院作报告。报告回顾2024年工作，指出面对外部压力加大、内部困难增多的复杂严峻形势，全年经济社会发展主要目标任务顺利完成，国内生产总值达134.9万亿元、增长5%，城镇新增就业1256万人，居民消费价格上涨0.2%，粮食产量首次跃上1.4万亿斤，新能源汽车年产量突破1300万辆，嫦娥六号实现人类首次月球背面采样返回；同时坦承内需不振、预期偏弱等问题交织叠加。报告提出2025年经济社会发展总体要求与主要预期目标，部署大力提振消费、因地制宜发展新质生产力、深入实施科教兴国战略、推动标志性改革举措加快落地、扩大高水平对外开放、有效防范化解重点领域风险、着力抓好三农工作、协同推进降碳减污扩绿增长、加大保障和改善民生力度、维护国家安全和社会稳定等十大任务，整体基调为坚持稳中求进、迎难而上，高质量完成“十四五”规划目标任务。
+# 核心政策
+## 核心政策
+### 2025年经济社会发展主要预期目标
+- **国内生产总值增长5%左右**，既是稳就业、防风险、惠民生的需要，也有经济增长潜力和有利条件支撑，并与中长期发展目标相衔接
+- **城镇调查失业率5.5%左右**，**城镇新增就业1200万人以上**
+- **居民消费价格涨幅2%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡
+- **粮食产量1.4万亿斤左右**，**单位国内生产总值能耗降低3%左右**，生态环境质量持续改善
+### 宏观政策取向
+- **财政政策**：今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；拟发行超长期特别国债**1.3万亿元**，更大力度支持`两重`建设；拟发行特别国债**5000亿元**支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**
+- **货币政策**：实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配
+- **民生导向**：强化宏观政策民生导向，经济政策的着力点更多转向惠民生、促消费，推动更多资金资源投资于人、服务于民生
+- **政策协同**：健全和用好宏观政策取向一致性评估工作机制，提升政策目标、工具、时机、力度、节奏的匹配度，注意倾听市场声音
+### 扩大内需与产业发展政策
+- 实施`提振消费专项行动`，制定提升消费能力、增加优质供给、改善消费环境专项措施；安排超长期特别国债**3000亿元**支持消费品以旧换新
+- 扩大有效投资：今年中央预算内投资已安排**7350亿元**；优化地方政府专项债券管理机制，支持和鼓励民间投资发展
+- 培育壮大新兴产业、未来产业：开展`新技术、新产品、新场景大规模应用示范行动`，培育生物制造、量子科技、具身智能、6G等未来产业
+- 推动传统产业改造升级：深入实施`制造业重大技术改造升级和大规模设备更新工程`，加快制造业数字化转型
+- 激发数字经济创新活力：持续推进`人工智能+`行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用
+### 科教兴国与改革开放政策
+- 加快建设高质量教育体系：制定实施`教育强国建设三年行动计划`，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，**逐步推行免费学前教育**
+- 推进高水平科技自立自强：加快组织实施和超前布局重大科技项目，加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目
+- 推动标志性改革举措落地：高质量完成`国有企业改革深化提升行动`，开展`规范涉企执法专项行动`，纵深推进全国统一大市场建设，综合整治`内卷式竞争`，修订出台新版市场准入负面清单
+- 深化财税金融体制改革：开展中央部门`零基预算改革试点`，加快推进部分品目消费税征收环节后移并下划地方，大力推动中长期资金入市
+- 扩大高水平对外开放：扩大电信、医疗、教育等领域开放试点，推动高质量共建`一带一路`走深走实，持续扩大面向全球的高标准自由贸易区网络
+### 风险防范与民生保障政策
+- 推动房地产市场止跌回稳：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，加快构建房地产发展新模式
+- 稳妥化解地方政府债务风险：完善和落实`一揽子化债方案`，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，坚决遏制违规举债行为
+- 积极防范金融领域风险：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险
+- 稳定和扩大就业：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，开展大规模职业技能提升培训
+- 强化基本医疗卫生服务：深化以公益性为导向的公立医院改革，优化药品集采政策，严格医保基金监管
+- 完善社会保障：**城乡居民基本养老金最低标准再提高20元**，适当提高退休人员基本养老金；制定促进生育政策，**发放育儿补贴**，大力发展托幼一体服务
+### 绿色转型与三农政策
+- 协同推进降碳、减污、扩绿、增长：持续深入推进蓝天碧水净土保卫战，全面推进以国家公园为主体的自然保护地体系建设
+- 积极稳妥推进碳达峰碳中和：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度，加快建设沙戈荒新能源基地，开展煤电低碳化改造试点示范
+- 增强粮食等重要农产品稳产保供能力：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`
+- 巩固拓展脱贫攻坚成果：提高监测帮扶效率，确保不发生规模性返贫致贫，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度
+- 推进农村改革发展：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围
+# 重点工作
+## 大力提振消费、提高投资效益，全方位扩大国内需求
+- **提振消费专项行动**：制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力，多渠道促进居民增收
+- **消费品以旧换新**：安排超长期特别国债3000亿元支持消费品以旧换新
+- **扩大服务消费**：扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力
+- **消费者权益保护**：强化消费者权益保护，营造安心放心消费环境
+- **扩大有效投资**：发挥好各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目，管好用好资金，坚决防止低效无效投资
+- **投资安排**：今年中央预算内投资已安排7350亿元；用超长期特别国债更大力度支持"两重"建设
+- **民间投资**：优化地方政府专项债券管理机制，支持和鼓励民间投资发展，让民间资本有更大发展空间
+## 因地制宜发展新质生产力，加快建设现代化产业体系
+- **培育新兴产业、未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动
+- **未来产业布局**：培育生物制造、量子科技、具身智能、6G等未来产业
+- **产业统筹与创新企业培育**：加强产业统筹布局和产能监测预警，梯度培育创新型企业，让更多企业在新领域新赛道跑出加速度
+- **传统产业改造升级**：深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型，开展标准提升引领传统产业优化升级行动，打造名品精品经典产业
+- **数字经济创新**：持续推进"人工智能+"行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端
+- **数字基础设施**：扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展
+## 深入实施科教兴国战略，提升国家创新体系整体效能
+- **高质量教育体系建设**：制定实施教育强国建设三年行动计划，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育
+- **高等教育与教师队伍**：扎实推进优质本科，加快"双一流"建设；建设高素质专业化教师队伍，加强师德师风建设
+- **科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革
+- **产学研融合**：加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目
+- **科技成果转化**：健全科技成果转化支持政策和市场服务，加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境
+- **人才队伍建设**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革
+## 推动标志性改革举措加快落地，更好发挥经济体制改革牵引作用
+- **国有企业改革**：高质量完成国有企业改革深化提升行动
+- **民营经济发展**：扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动
+- **全国统一大市场建设**：破除地方保护和市场分割，综合整治"内卷式"竞争，修订出台新版市场准入负面清单，优化新业态新领域市场准入环境
+- **信用与退出机制**：构建统一的信用修复制度，完善企业简易注销，逐步推广新主体活动发生地统计
+- **财税体制改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方
+- **资本市场改革**：深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设
+## 扩大高水平对外开放，积极稳外贸、稳外资
+- **稳定对外贸易**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设
+- **外贸新增长点**：拓展境外经贸合作区功能，支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点
+- **吸引外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，加强外资企业服务保障
+- **自贸试验区建设**：推动自贸试验区提质增效和扩大改革任务授权，持续营造市场化、法治化、国际化一流营商环境
+- **共建"一带一路"**：统筹推进重大标志性工程和"小而美"民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局
+- **多双边和区域经济合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制
+## 有效防范化解重点领域风险，牢牢守住不发生系统性风险底线
+- **房地产市场止跌回稳**：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，有序搭建相关制度
+- **房地产发展新模式**：加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子
+- **地方政府债务风险化解**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作
+- **政府债务管理**：完善政府债务管理机制，坚决遏制违规举债行为
+- **金融领域风险防范**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险
+- **金融监管体系**：健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案，有效维护金融安全稳定
+## 着力抓好"三农"工作，深入推进乡村全面振兴
+- **粮食稳产保供**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设
+- **种业振兴与农机装备**：深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广
+- **巩固拓展脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫，加强易地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度
+- **帮扶制度完善**：统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系
+- **农村改革发展**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围
+- **兴业强县富民**：因地制宜推动兴业强县富民一体发展，拓宽农民增收渠道，持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村
+## 推进新型城镇化和区域协调发展，进一步优化发展空间格局
+- **农业转移人口市民化**：科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务
+- **随迁子女与住房保障**：强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道
+- **城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市
+- **区域战略实施**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极
+- **区域产业协作**：支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东中西、东北地区产业协作
+## 协同推进降碳、减污、扩绿、增长，加快经济社会发展全面绿色转型
+- **污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程
+- **美丽中国先行区建设**：积极推进美丽中国先行区建设，不断满足人民群众对良好生态环境的新期待
+- **绿色低碳经济**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用
+- **绿色消费机制**：健全绿色消费激励机制，推动形成绿色低碳生产方式和生活方式
+- **碳达峰碳中和**：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度
+- **能源与气候治理**：加快建设沙戈荒新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理
+## 加大保障和改善民生力度，提升社会治理效能
+- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换
+- **就业创业服务**：优化就业创业服务，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障
+- **职业技能培训**：开展大规模职业技能提升培训行动，让多劳者多得、技高者多得、创新者多得
+- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程
+- **药品集采与医保监管**：优化药品集采政策，强化质量评估和监管；健全药品价格形成机制，支持创新药发展；完善中医药传承创新发展机制；严格医保基金监管，让每一分钱都用于增进人民健康福祉
+- **社会保障**：城乡居民基础养老金最低标准再提高20元，适当提高退休人员基本养老金
+- **养老服务**：推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、辅助器具购置和租赁支持力度
+- **生育支持**：制定促进生育政策，发放育儿补贴，大力发展托幼一体服务
+- **社会救助**：完善分层分类社会救助体系，保障困难群众基本生活
+- **精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业，推动优质文化资源直达基层
+- **全民健身**：推进群众身边的运动场地设施建设，广泛开展全民健身活动，加强青少年科学健身和健康干预
+- **国家安全和社会稳定**：全面贯彻总体国家安全观，深入实施安全生产治本攻坚三年行动，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对
+- **基层治理与法律服务**：推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国
+## 政府自身建设与国防外交
+- **"十五五"规划编制**：今年将开展"十五五"规划编制工作，科学确定发展目标，谋划好重大战略任务、重大政策举措、重大工程项目
+- **法治政府建设**：严格依照宪法法律履职尽责，自觉接受同级人大及其常委会监督、人民政协民主监督、社会和舆论监督，加强审计监督
+- **行政效能提升**：把面向基层的督查检查考核减下来，让广大干部把更多时间和精力用到干实事上
+- **民族团结与宗教侨务**：以铸牢中华民族共同体意识为主线，推进民族团结进步事业；坚持党的宗教工作基本方针，积极推进我国宗教中国化；完善侨务工作机制
+- **国防和军队建设**：贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全力打好实现建军一百年奋斗目标攻坚战，深入推进练兵备战，协力推进跨军地改革
+- **港澳工作**：全面准确、坚定不移贯彻"一国两制"、"港人治港"、"澳人治澳"、高度自治的方针，落实爱国者治港、爱国者治澳原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局
+- **对台工作**：坚持一个中国原则和"九二共识"，坚决反对"台独"分裂和外部势力干涉，推动两岸关系和平发展，完善促进两岸经济文化交流合作机制和政策
+- **外交工作**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，推动落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10273/7336</t>
         </is>
       </c>
     </row>
@@ -12264,6 +12454,58 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议为景城苑小区物业招标答疑会，业主代表就改造计划、停车管理、承接查验、安防停车、杂物晾晒等问题向两家投标物业公司（富家物业、知名管理）提问，两家公司分别作答。富家物业预计改造在一年内完成，针对停车乱象先分析原因再制定措施，承接查验提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先与现物业私下沟通，必要时在业委会或街道社区许可下采取强制措施；安防改善包括增设人行门禁、升级大堂报到系统、增设隔离墩、建设外围停车场并安装停车管理系统、增设电动车停车场。知名管理成立于2004年，总部在深圳，全国367个项目、127个业委会项目；团队编制16人，薪酬福利高于周边同类项目，一线人员不外包；进场第一个月集中资源进行环境绿化清洁整改，半年内排查设备设施，八个月内保证项目有效运作；包干制下保证财务透明，每季度公示物业管理费和停车费；承接查验前与社区街道派出所沟通，与现物业和业委会明确设备设施和债务债权，增派150%人员；安防措施包括关键岗位用老员工、收集业主车辆信息、制定停车管理方案、升级门禁系统；针对楼层杂物采取宣传引导、联合社区、沟通限期处理、提供临时堆放区，强调疏导而非强制；针对晾晒问题计划设置集中晾晒区，提供免费上门晾晒服务。评标委员会打分后，主持人宣布各公司得分：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源新东源物业管理有限公司54.48分，中标候选人为深圳市资平物业发展有限公司。打分环节全程保密，暂停网络直播，录像材料不予公开；总评委打分去掉一个最高分和最低分。
+# 分段速览
+## 00:00:10-00:09:25 富家物业答疑
+业主代表首先提问富家物业若中标后从哪些方面改善小区现状及预计时间，发言人1回应称具体改造项目已在标书117页详细说明，预计改造时间在一年内完成。随后业主代表反映考察中发现卫生室存在车辆停放不规范、电动车乱停现象，发言人1表示应先分析乱停原因，若是停车位不够则增加停车位，若是业主不自觉则派保安、客服人员现场说服劝阻纠正。第三个问题关于承接查验工作，发言人1介绍富家物业有丰富二手小区交接经验，提前两周项目负责人入场摸底，提前一周服务人员到位培训，交接不畅时先与现物业私下沟通，无法解决则请业委会或街道社区组织协调会，仍无法解决则在获得许可下采取强制措施。第四个问题涉及监控门禁失效导致人员车辆随意进出及停车混乱，发言人1提出五项措施：大门口增设人行门禁系统、升级大堂报到系统、增设隔离墩、建设外围停车场并安装停车管理系统、增设电动车停车场。最后一个问题关于类似项目管理经验及满意度与收费率措施，发言人1表示没有与景城苑很相似的小区，处理问题采用四句话：用心倾听、如实记录、马上处理、及时反馈。
+## 00:09:36-00:12:22 评标流程说明
+业主代表宣布深圳市资平物业发展有限公司代表上场，并说明抢标时间为10分钟，每道题答题时间为3分钟。评标流程为各投标公司依次答辩后由评标委员会打分。
+## 00:12:22-00:19:44 知名管理公司介绍与答疑
+知名管理发言人介绍公司成立于2004年，总部在深圳，是全国市场化物业公司，无开发背景，目前全国有367个项目，其中127个为业委会项目。公司创始人陈志平先生原为万科物业创始人，曾协同建立中国第一个业委会。公司为中国物业管理协会副会长单位、全国百强企业。针对景城苑项目，公司打造"让一线权利归还业主"理念，确保财务透明和管理透明，包干制下每季度公示物业管理费和停车费。团队编制16人，薪酬福利高于周边同类项目，一线人员不外包。进场第一个月调动湖南战队其他项目资源进行环境绿化清洁全面清扫，半年内调动集团设备公司工程师对设备设施全面排查诊断，八个月内保证项目有效运作。公司导入顾客管理系统集中处理业主投诉咨询报事，形成大数据库管理业主咨询投诉，并针对老龄化开展社区文化活动，每两个月开展一次。
+## 00:19:52-00:34:44 知名管理答疑
+业主代表提问若知名管理中标后如何改造小区及预计时间，发言人回应经查勘主要存在安全管控、设备设施维护、环境、社区氛围四方面问题，进场第一个月集中资源整改环境绿化，半年内排查设备设施，八个月内达到有序状态，一年内保证小区整体有序。第二个问题关于包干制经验及公益性拓展服务，发言人介绍公司在长沙有11个项目，其中10个为包干制，强调包干制下保证业主知情权、增加与业委会互动、团队直招，管理干部30%来自现有团队、60%左右来自现有物业优秀员工或重新招聘；公益性服务包括居家上门免费服务、家政、24小时业主护送服务等。第三个问题关于承接查验，发言人表示前期准备要充足，与社区街道派出所沟通，与现物业和业委会明确设备设施和债务债权，按专业线分专业组查验，调动集团工程师协助，增派150%人员。第四个问题关于安防停车，发言人提出关键岗位用老员工保证责任心，收集业主车辆信息制定停车管理方案，升级门禁系统识别外来人员，通过技术手段梳理把控监控。第五个问题关于楼层顶层堆放杂物和乱搭乱晒，发言人强调宣传引导、联合社区应急管理部门、上门沟通限期处理、提供临时堆放区，强调疏导而非强制；针对晾晒问题计划设置集中晾晒区，提供免费上门晾晒服务。
+## 00:35:00-00:35:28 评标结果公布
+业主代表宣布所有答辩结束，评标委员会进行打分，打分环节全程保密，暂停会场网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。随后公布各公司得分：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源新东源物业管理有限公司54.48分，中标候选人为深圳市资平物业发展有限公司，招标活动圆满结束。
+# 要点梳理
+## 富家物业答疑
+- **改造计划**：富家物业预计改造时间在一年内完成，具体12大改造点已在标书第117页详细说明。
+- **停车乱象应对**：先分析乱停原因（场地不足、距离远或不自觉），若车位不足则增加停车位，若业主不自觉则派保安、客服现场说服、劝阻、纠正。
+- **承接查验安排**：提前两周项目负责人入场摸底小区现场情况；提前一周服务人员到位并培训公司制度与操作流程。
+- **交接不畅应对**：先与现物业私下沟通了解诉求，公司间能解决则解决；无法解决则请业委会或街道社区组织现场协调会；仍无法解决时，在业委会、业主大会及街道社区许可下采取强制措施。
+- **安防改善措施**：大门口增设人行门禁系统（支持手机微信、卡、密码进出）；升级大堂报到系统，录入业主车辆信息统一管理，临时车辆由安保登记后放行；地面增设隔离墩禁止公共场所停车，保障消防通道与人行通道畅通；建设外围停车场并安装停车管理系统；小区内增设电动车停车场。
+- **业主问题处理原则**：采用「用心倾听、如实记录、马上处理、及时反馈」四句话，处理完成后及时向业主反馈完成时间。
+## 知名管理答疑
+- **公司背景**：知名管理成立于2004年，总部在深圳，为全市场化物业公司，无开发背景；全国367个项目，其中127个为业委会项目；公司创始人陈志平为万科物业创始人，曾协同建立中国第一个业委会；公司为中国物业管理协会副会长单位、全国百强企业。
+- **团队配置**：景城苑项目团队编制16人，薪酬福利保证高于周边同类项目；所有一线人员直招不外包。
+- **进场改造计划**：四步举措——第一步「洗理静音」，进场第一个月调动湖南战队其他项目人员资源，对小区环境、绿化、清洁、杂物进行全面清扫；第二步「疏金活选」，调动集团设备公司水电、给排水、电梯、消防工程师对设备设施全面排查诊断，在投资范围内集中改造；第三步「疑难杂症」，涉及消防、渗水等重大事项检查后提供意见，经业委会授权或业主大会招投标；第四步「有效提升」，将总部管理标准与经验延续至本项目，八个月内保证项目有效运作。
+- **包干制经验**：长沙11个项目中10个为包干制、1个为酬金制；包干制下保证财务透明，每季度公示物业管理费、停车费；管理透明，业委会授权事项推进业主代表参与公共事务管理；团队30%管理干部从现有人员选拔，60%左右为现有物业优秀员工或重新招聘。
+- **公益与增值服务**：长沙项目居家上门服务员工免费，材料费由业主自买或物业代购；开展家政、24小时业主护送服务等有偿与无偿业务。
+- **承接查验安排**：前期与社区、街道、派出所沟通；与现物业、业委会明确设备设施、债务债权；按专业线分专业组验收，委派集团工程师协助查出问题；在现有16人团队基础上增派150%人员参与承接查验。
+- **安防与停车管理**：门岗、门勤岗、车务等关键岗位用老员工，对来访人员与车辆进行管控、登记、核实后放行；收集小区业主车辆信息，制定整体停车管理方案（含禁区停放、动线规划）；升级门禁系统识别外来人员与业主亲戚来访；通过设备公司技术手段对关键岗位与关键部位监控进行梳理把控。
+- **楼层杂物处理**：通过上门宣传、海报、法律知识宣传引起业主重视；与社区、应急管理部门联合行动；逐户沟通说明危害，给予业主处理杂物的时间段；可提供闲置区域供业主临时堆放并限期解决；强调「疏导而非强制」，避免激发矛盾。
+- **晾晒问题处理**：计划在小区寻找位置设置集中晾晒区；可提供免费增值服务，太阳大时物业工作人员上门取送晾晒物品（早上拉出、晚上拉回）。
+## 结论与决定
+- **评标结果**：评标委员会打分后确定中标候选人为深圳市资平物业发展有限公司。
+- **各公司得分**：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源新东源物业管理有限公司54.48分。
+- **打分规则**：总评委打分去掉一个最高分和一个最低分；打分环节全程保密，暂停会场网络直播，录像材料不予公开。
+## 待确认与风险
+- **停车管理**：小区存在车辆停放不规范、电动车乱停现象，卫生室区域同样存在此类问题。
+- **安防隐患**：监控门禁失效导致人员车辆随意进出，小区停车管理混乱。
+- **消防通道占用**：消防通道停放车辆较多，含业主车辆及外来车辆。
+- **楼层杂物**：楼层顶层存在堆放杂物或乱搭乱晒问题，涉及业主生活与安全影响。</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11743/4252</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="13.5" customHeight="1" s="9">
       <c r="A35" s="6" t="inlineStr">
@@ -12379,6 +12621,63 @@
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本期视频由主讲人李正（B站「正直讲史」）讲述康熙朝文渊阁大学士陈廷敬的一生，形式为历史人物专题讲解。视频旨在澄清影视剧与史实的差异——剧中陈廷敬支持撤藩、招抚台湾、征剿噶尔丹等功绩均非史实，但康熙临终前仍询问大臣中学问人品如陈廷敬者可代理内廷事务者为谁，由此引出其生平。内容按三个阶段展开：妈妈张氏的开蒙、圣祖康熙的讲师、至公无私的落幕。核心主张有三：其一，陈廷敬虽无影视剧中的显赫功绩，却凭清廉正直与恪守初心赢得康熙终身信任；其二，其童年由母亲张氏开蒙，6岁前已背诵《论语》《孟子》《大学》《中庸》《诗经》，天赋与家教奠定一生根基；其三，宦海浮沉50年声名清白，历经张谦案诬陷仍获康熙力挺复出，印证「清者自清」。关键锚点包括：陈廷敬1638年生于山西泽州府阳城县，21岁中进士入翰林，75岁病逝谥号文贞。对听众而言，本讲以具体人物案例展现清代官场生态与个人操守的张力，适合对清史、古代政治人物及廉政主题感兴趣的观众。
+# 核心观点与论证
+## 母亲张氏开蒙奠定根基
+- **开蒙方式**：陈廷敬6岁外出上学前，由母亲张氏口授背诵《论语》《孟子》《大学》《中庸》《诗经》，史载“凡四子书毛诗皆太夫人口授以诵”。
+- **母亲背景**：张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，史载“太夫人少儿颖慧特异……无不背诵通晓大义”；嫁后“于家政稍暇即出书籍……非秉夜不归寝”。
+- **鼓励教育**：陈廷敬9岁作《咏牡丹》，其中“要使误接春”一句被母亲赞为“天才”，童年学习大半在母亲关照下展开。
+- **科举成绩**：顺治八年（1651年）14岁以全省第一考中秀才；20岁中举人，21岁中进士并入翰林院任庶吉士，同年入选翰林院。
+## 御赐改名化解重名风波
+- **重名事件**：顺治15年（1658年）四月，山西泽州陈敬与直隶通州陈敬同届中进士入翰林院为庶吉士，因满汉双语文件与考试造成混淆。
+- **他人连累**：直隶陈敬因满文考试不及格被顺治点名批评并罚俸一年，原话“陈敬……清书俱未习熟……着各罚俸一年”，因未带籍贯导致风言风语波及陈廷敬。
+- **主动改名**：陈廷敬22岁主动上书请更名，史载“庶吉士陈敬奏请更名廷敬，以与直隶庶吉士陈敬同名故也”。
+- **御赐之名**：据李光地说，“廷”字为顺治所赐，原话“陈文贞公初名敬，其家廷字文选日张皇帝所赐也”，改名后与顺治拉近关系。
+## 康熙讲师与教学风格
+- **仕途晋升**：康熙六年（1667年）考察一等称职；两年后32岁升任正六品国子监司业；34岁升从四品翰林院侍讲学士；35岁充日讲起居注官；39岁充经筵讲官。
+- **整顿国子监**：陈廷敬任国子监司业时废除学生拜见须带见面礼的不成文规定，史载“凡诸生以至献者悉秉去之”，学生不送礼才愿意见。
+- **教学风格**：讲评经史“特别狠辣，对就骂错就骂”，曾指史书痛骂孙权背刺关羽，原话“全其屯权也哉”，康熙欣赏其坚定三观与外放风格。
+- **执掌翰林院**：康熙16年（1677年）正月任翰林院掌院学士，教习当届庶吉士。
+## 至公无私整顿吏治
+- **捐纳考试**：康熙23年（1684年）47岁任左都御史，上奏捐纳买官者正式上岗须追加考试，“文艺略小者给予录用，否则且令异业听其再试”；吏部反对称“以前补用人员从未考试，应不准行”，康熙支持并令各地督抚详查已任命官员，“凡临民之官内有不识字义者，着该督府不时实行查参修治”。
+- **全面弹劾**：针对各省督府作风问题、地方政府赈灾懒政问题严查弹劾，并亲自拟定新的赈灾报批流程；两年内连续出任工部、户部、吏部三部尚书，所到之处整顿得罪人。
+- **个人立场**：面对“官场里不和光同尘会落满怨”的劝告，陈廷敬表示“我贤与虽折且怨，庸和尚说”，只要人是对的、事是好的，遭受挫折埋怨也无所谓。
+## 张谦案与清白复出
+- **被诬受贿**：康熙26年（1687年），湖广巡抚张谦（陈廷敬老乡兼亲家）贪污被抓，供称曾贿赂徐乾学、高士奇及陈廷敬，证据是三人曾写信劝其好好当官，被张谦解读为索贿暗示。
+- **自辩与辞官**：陈廷敬称“前楚府一案者……积疑成恨，羽射连染”，因对张谦疏远反遭怨恨攀咬；51岁主动上书辞官，康熙准许但留京修书。
+- **康熙定调**：康熙传旨主审官马齐“此时需旧款需问，不可蔓延，若蔓延则千累者重”，只处理张谦一人，其余事后密查。
+- **清白佐证**：主讲人给出三点理由——据李光地说张谦案从索贿到举报皆徐乾学一手策划；徐乾学贪污事迹多且热衷结党；徐乾学、高士奇后来均因贪污被罢官，唯独陈廷敬康熙29年（1690年）53岁复出再任左都御史，康熙以任命全国最高监察长官宣告其清白。
+## 晚年请退与身后哀荣
+- **官至大学士**：康熙42年（1703年）66岁升任文渊阁大学士，同时总理南书房事务，是内阁中唯一既管南书房又任经筵讲师的大学士。
+- **四次请退**：70岁起连续三年三次申请退休均被康熙拒绝，康熙称“机务重地，良难其人，不必求去”；73岁第四次申请获准。
+- **御赐匾联**：康熙赐匾额“午亭山村”和楹联“春归乔木浓阴茂，秋到黄花晚”，并称“自此不与人写字矣”。
+- **病逝与厚葬**：康熙49年（1710年）后两年，陈廷敬75岁病逝，谥号文贞；康熙包办治丧费用，从大内取紫砂碗做棺材，命皇三子允祉及大臣侍卫往吊，令各部院满汉大臣往吊。
+# 金句总结
+&gt; 朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？
+- 康熙在陈廷敬临终前询问，还有谁可代理内廷事务，足见对其倚重之深。
+&gt; 自古未有不晓文艺之人可以为民父母者也，有未经考职遂行捐纳者，于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试。
+- 陈廷敬任左都御史时上奏，主张捐纳买官者正式上岗前必须追加考试，获康熙支持。
+&gt; 臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节。
+- 张谦案中被攀咬后，陈廷敬主动上书辞官以证清白。
+&gt; 苟正其身矣，于从政乎何有？
+- 主讲人引《论语》总结陈廷敬一生：自身品行端正，治理政事便无困难。
+&gt; 我贤与虽折且怨，庸和尚说只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，你也是无所谓的。
+- 有人劝陈廷敬官场应和光同尘时，他回应只要行得端做得正，不怕挫折与埋怨。
+# Q&amp;A 环节
+未提及</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>9132/2677</t>
         </is>
       </c>
     </row>
@@ -12996,6 +13295,68 @@
           <t>采访记录</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t># 访谈概述
+本期《锵锵三人行》围绕刚播完的日剧《大奥》与明朝历史展开，受访者为《明朝那些事》作者当年明月（笔名），与主持人及另一位嘉宾共同探讨中日文化差异与历史认知。访谈主线分两大板块：一是由《大奥》切入日本文化，覆盖该剧反映的日本历史阶段、大奥制度、日本民族精神中的极端精神与忠诚文化、战后经济崛起及中日文化差异；二是转向明史，讨论明史为何吸引人、朱元璋的历史地位、明朝兴亡经验、晚明市民生活及明式家具等话题。受访者核心观点包括：日本文化强调极端精神，做事做到尽头，战后仅用30年成为世界第二经济强国（绝对量而非人均量），是强国中唯一没有资源的国家；中国文化的核心精神是中庸，日本则坚持做到极致，二者差异巨大；历史事件发生时有背景，后人并不比前人聪明，「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」。访谈看点在于当年明月以《大奥》为引，结合其亲历的日本豆腐厂参观（夜里12点整准时开工）等细节，指出日本人的严谨与忠诚文化，并直言正德皇帝「绝不是史料上所写的那么蠢」，认为其被嘉靖朝修史者写坏。
+# 访谈详细记录
+## 日剧《大奥》与日本文化
+- **《大奥》历史阶段**：受访者认为该剧三部曲中，前两部大致对应中国晚清到清初时段，第三部在明治维新之前，是一部有跨越性的历史剧。
+- **大奥释义**：受访者指出大奥即普通话所说的后宫，日语中"奥"指很深的地方，即屋子最里处，如"深奥"一词仍保留此痕迹。
+- **日本极端精神**：受访者认为从《大奥》可看出日本文化从头到尾未变，其特点是"极端精神"——所有事情要做到尽头，如剧中所有演员达成一致、人人认真，具有专业精神。
+- **战后经济奇迹**：受访者认为日本战后用30年成为世界第二经济强国（绝对量而非人均量），不是偶然而是必然，源于全民族极端精神；日本是世界上强国里唯一没有资源的国家。
+- **忠诚文化体现**：受访者以剧中阿福为例——25岁进大奥当奶妈，65岁去世，40年无论做什么事不处私心、完全是公心，被伤害的对方都认为他出于公心，这是日本忠诚文化的具体体现。
+- **豆腐厂细节**：受访者讲述参观日本最底层豆腐厂的经历——规定当天做当天卖，夜里11:45所有人坐等看表，12点整准时开工，4点多干完上市，无人闲聊胡侃。
+- **做绳子的商人**：受访者举例日本做绳子做到全日本第一的人，几年内不赚钱，从批发到送货1分钱不赚，等铺平市场后拿单据要求加2%，全国加起来4%即挣大钱。
+- **中日文化差异**：受访者认为中国文化精神是中庸，讲究融合、走最适合的路；日本精神恰恰相反，坚持一个原则做到极致，如炮手忘记一切只记得把炮开出去即达最高境界。
+- **终身雇佣制**：受访者指出日本实行终身雇佣制，按经济学原理缺乏竞争应导致低效，但日本终身雇用下效率依然特别高，是经济学上的奇迹。
+- **日本生存环境**：受访者认为日本没有资源、常火山地震，人对世界有极强求生欲望或悲观感，必须融入团体按固定规则做事才能生存；受访者认为日本"聪明人"没有生存环境，社会文化抵制非常难过。
+- **对死亡的看法**：受访者认为日本人看樱花只看落的那天，因岛国生态环境恶劣，对死亡不是藐视而是有点向往或不惧怕，二战日军在华暴行源于藐视生命；另一受访者不同意，认为日本民族不是藐视生命而是重视，经济危机时很多身家万贯者选择自杀。
+- **是否愿做日本人**：受访者表示不愿做日本人，因其很多时候像盲从，且有寻死的潜在欲望；另一受访者认为每个人在自己文化环境里愿意做，但做不成，因为自己的文化不允许这种现象生存。
+## 明朝历史与《明朝那些事》
+- **写明史的原因**：受访者（当年明月）表示写明朝是因为明史资料最多；历史研究有两个难点，一是先秦（如孙武事迹在史记仅一两篇，多为编撰），二是明清——明史录几千万字、明通鉴、明史记事本末、明会典等堆得比山还高，但一个事件可能有七个不同说法，如同罗生门。
+- **明朝的跌宕起伏**：受访者认为明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变（皇上被瓦剌军抓走）、夺门之变等，各种"之变"特别多，构成现代版电视剧般离奇情节。
+- **推崇朱元璋**：受访者认为朱元璋是历史上唯一由最底层（乞丐）当上皇帝的人，刘邦好歹算村长或乡长；要过饭的人当上皇帝，每一层的猫腻全知道，因此疑心重；明朝规章制度由朱元璋定下，基本无大改动。
+- **英雄史观**：受访者认为人的因素最大，改变时势一定出现一个人；朱元璋天分相当高，如同《亮剑》中李云龙没上过军事院校却能打仗，是战场上死死生生积累的经验。
+- **朱元璋起义的逼上梁山**：受访者讲述朱元璋原在庙里犹豫是否参加起义军，因信差送信被人听到告发，没办法只能去起义；受访者强调历史最重要的是明白它是发生过的，旁观者觉得好玩，但当事人是掉脑袋的风险。
+- **历史经验教训**：受访者认为"我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训"，因为历史事件发生时有背景，你不比前人聪明，甚至可能比前人笨，那种情况出现时你也得这么办。
+- **史书如照片**：受访者比喻史书记载下来的是照片，而古人的生活是录像，你不知道那一幕之前和之后是什么，所以不能套用历史经验教训。
+- **晚明市民生活**：受访者认为明末很多真相被掩盖，江南一带市民生活特别轻松，想去哪去哪，皇册都不用，给人当雇工，工商业兴起，三言二拍这类市民小说出现说明有养活自己的资本；李自成起义时陕西一带发生大规模灾荒。
+- **明末工艺与艺术**：受访者指出明末工艺品变得非常精细，日本派大量工匠来交流学习；吴门画派文徵明、唐寅等画小桥流水、风雨归舟图，充满欣赏感觉，说明生活好；到八大山人朱耷时画翻白眼，因对社会愤愤不平。
+- **明朝灭亡的蹊跷**：受访者提到1644年明朝灭亡那年北京闹瘟疫（疙瘩瘟，可能是天花），李自成打到京城无人抵抗；受访者与老师交流认为明朝亡得真蹊跷，什么坏事都赶上了。
+- **王朝300年大限**：受访者认为中国历史王朝300年是大限，逼近300年自己就没了，和人到八九十岁大限快到一样；严格讲超过300年的只有宋朝（南北宋接上，退让大半个国土），汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
+- **明朝的趣味**：受访者认为明朝什么都有——宦官专政（魏忠贤）、文官专政（张居正）、皇帝专政（朱元璋），皇帝出去了还能回来、回来了还能做皇帝；吴三桂与满清合作入关，除陈圆圆外还因崇祯死了，当时说法是"入关为崇祯皇帝复仇"。
+- **正德皇帝被写坏**：受访者认为正德皇帝（明武宗）被写坏是因为接班的嘉靖不是他儿子而是堂兄弟，嘉靖不能把他写太好；明武宗实录是嘉靖指派杨廷和等人编的，有偏颇；正德从江南回来在通州先停半年，先派人打探京城有没有埋伏，说明他很有城府，绝非史料所写那么蠢。
+- **正德与天启轶事**：受访者讲述正德要去江南，大臣跪金水桥前抗议，锦衣卫打死十几个；到扬州要东西不给，让人准备酒席又说吃不了，把酒席折合银两带回去，皇帝打秋风；另一受访者补充天启皇帝爱当木匠，干完活拆大盆去卖，卖完还打听卖得怎么样，成就感特大。
+- **明式家具地位**：受访者认为天启当木匠从侧面反映当时社会时尚，家具在每个人心里地位高，明式家具在国际上地位高绝非偶然，"所有的偶然中一定有个必然的因素"。
+- **明清审美差异**：受访者认为宋明是典型汉人政权、文人政权，文人审美较高，对美的判断不是表象的；满族是异族，进来后对美的判断都是表象的——今天凡是外在直观能看到的都卖得贵，而晚清到民国初年值钱的一定是素雅的。
+# 关键引语与金句
+&gt; “慢慢来才是最快的方法。”
+- 当年明月在讨论日本文化中“不夹杂私心、按自己本分做事”时引述他人观点，用以说明不偷奸耍滑反而更有效率。
+&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
+- 当年明月回应主持人关于明朝兴亡经验教训的提问，指出历史事件有特定背景，不能简单套用经验。
+&gt; “你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办。”
+- 当年明月解释为何不能从历史中轻易吸取教训，强调后人常误以为前人愚蠢，实则身处同样情境未必做得更好。
+&gt; “史书上记载下来的是什么？照片。而我们实际上生活、古人的生活都是录像。”
+- 当年明月说明史书只记录瞬间而缺乏前因后果，导致人们对历史产生误解。
+&gt; “一个人到战场上死死生生多少年，没死，最后积累下来经验……我一上战场我就知道，敌人会往哪走，我该怎么打。”
+- 当年明月以《亮剑》中李云龙为例，说明朱元璋这类人物靠实战经验而非书本知识成就事业。
+&gt; “日本的精神就恰恰相反，他坚持一个原则……当他忘记所有的事情，只记得把这一炮开出去，他就达到了他的最高境界。”
+- 当年明月对比中日文化精神，说明日本文化追求极致、专注单一目标。
+&gt; “中国的文化精神是中庸……不是对也不是错，不是黑也不是白……而是一条最适合的路。”
+- 当年明月以马先生家具店中“硬木刻云彩”为例，阐释中国文化的中庸与融合精神。
+&gt; “日本战后用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然……他是世界上这个强国里唯一没有资源的国家。”
+- 当年明月在讨论日本民族极端精神时，以战后经济崛起为例论证其必然性。</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17496/3875</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="13.5" customHeight="1" s="9">
       <c r="A37" s="6" t="inlineStr">
@@ -13361,6 +13722,73 @@
           <t>采访记录</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t># 访谈概述
+余华接受访谈，回顾其写作生涯与创作理念。余华是中国当代作家，代表作包括《活着》《兄弟》《第七天》《文城》等。访谈围绕其写作生涯的1.0/2.0/3.0阶段、《兄弟》的创作与批评、对批评的态度与自我调节、中年危机、未来写作计划、对马尔克斯的反思、网络热度及人生感悟等话题展开。余华最核心的观点包括：其一，写作3.0版本（受威廉·福克纳影响，用视觉描写代替心理描写）以后就没再升级，因为写作已成熟；其二，他认为自己40多岁到50岁最好的写作时间浪费了，只出了两部作品，剩下的写作时间可能只有十年左右；其三，他不再追求高度，而是追求宽度，但也不排除最后一部作品创造新高度的可能性。访谈锚点包括《兄弟》（1996年开始创作，2003-2004年重写）、《第七天》及三亚。看点在于余华亲述童年被海流带走的经历，以及他澄清莫言在莎士比亚故居发誓要成为剧作家是「瞎扯」，并透露互联网上关于他说的话有一半不是他说的。
+# 访谈详细记录
+## 写作生涯的1.0/2.0/3.0阶段
+- **1.0阶段**：余华认为文学创作第一个重要时刻是逼自己坐下来写，让屁股和椅子建立友谊；他回忆若没有离开写字桌躺到床上幻想作品多么厉害，可能就不会去写它。
+- **2.0阶段**：受卡夫卡启发，写作越写越难，遇到心理表现的障碍；余华认为若写人物内心平静没有意思，内心动荡不安则写1万字也不够。
+- **3.0阶段**：受威廉·福克纳影响，采用视觉描写代替心理描写——让心脏停止跳动、让眼睛睁开；他举例《狂人日记》中"赵家的狗看了我一眼"，一下就知道人物精神状态。
+- **3.0以后未再升级**：余华认为3.0版本以后就没再升级，因为写作已成熟；《活着》虽可能被视为4.0版，但对他已不是难题，知道写没文化的农民必须用最朴素的语言。
+## 《兄弟》的创作与批评
+- **创作时间线**：《兄弟》创作始于1996年，因当时中国社会变化复杂而写；2003年和2004年重新拿回来写时，庆幸1996年没有写完，因为从2004年再看，96年时候的变化不算什么，那才是真正大的变化。
+- **出版期待与落差**：余华说《兄弟》出版时认为肯定是一片赞扬，带着这样的期待去，结果一片骂声，弄得他有点糊涂；当时互联网已形成浪涛，他努力想把骂声引过来，接受了很多采访去解释作品。
+- **《第七天》与《文城》的反响**：到《第七天》出来时余华只接受了一个采访，什么都不做让他们去骂；他提前告诉朋友们要做好思想准备，结果果然一片骂声；《文城》出来时骂声还有但少一点，他调侃"骂人的人也累"。
+## 对批评的态度与自我调节
+- **对待批评的方式**：余华认为第一就是不要去看，第二有些批评要重视；有些批评没有道理，比如批评宋凡平人物太完美——宋凡平是阶段性出现的人物，只能写他在这个阶段的表现，没有一个从头到尾贯穿的人物才需要写得丰富。
+- **有道理的批评**：余华认为"社会底层人也未必都那么善良"这句关于《第七天》的批评说得很好；他解释《第七天》必须把善良在死无葬身之地表现出来，否则没有力量，但写现实生活中的勾心斗角不能太邪恶，这种考虑会在以后写小人物时纳入。
+- **互联网上的误传**：余华说互联网上关于他说的话有一半不是他说的，比如"想要命好的"、"精神内耗就是心里的戏太多"都不是他说的。
+## 中年危机与自我调节
+- **34岁时的感受**：余华在年终总结中写道，一个成年人每到年底都会发现一种虚无；当时感觉生活每天都在呼吸，但人口增加了、孩子来了，空间并没有因此变得宽敞一点。
+- **中年危机的本质**：余华认为突然发现没有那么多新的东西，只有写作能够得到一些新的东西，虚构的世界带来新东西，而现实世界每天重复；这是所有人都会遇到的中年危机。
+- **自我调节方法**：余华建议面对负面消息太多时可以选择屏蔽不看，因为发生的事情我们无法选择什么让它发生，但可以选择什么让自己知道、什么让自己不知道；哪怕知道可能是真的，也可以选择不看。
+## 未来写作计划与对高度和宽度的追求
+- **浪费的时间与剩余时间**：余华认为自己40多岁到50岁最好的一段时间浪费掉了，只出了两部作品；他估计能够好好写作的时间可能还有十年左右。
+- **未完成的长篇小说**：余华提到2006年开始写的一部长篇小说，时间跨度跟《兄弟》一样，但从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式去写；现在身体状态可能还能维持这种激烈，但那个感觉没了，80年代和90年代的感觉都在远去，很难找回来。
+- **写作计划**：余华计划先写完一个喜剧，想改变读者对他的印象，让读者不再觉得这个人那么悲观；他提到开学时去和学生见面，处理学校事务后回到三亚继续写作，安安静静把感觉找回来。
+- **从追求高度转向宽度**：余华表示对高度已经不追求了，现在追求宽度；他认为作为作家能走到的高度就是现在的高度，允许自己下滑一下但不要下滑太多，年纪大了知道自己的能力在哪里、还有多少潜力；但也不排除运气来了在最后一部作品上创造新高度的可能性。
+## 对马尔克斯的反思与文学理想
+- **被马尔克斯误导的一代**：余华认为他们这一代中国作家在很大程度上都被马尔克斯误导，整整一代都想在一本书里写一个世纪的故事，但其实没有必要；托尔斯泰、狄更斯、莎士比亚、巴尔扎克、福楼拜、司汤达、契诃夫都是写自己时代的故事。
+- **对马尔克斯的补充看法**：余华认为马尔克斯开创了一个先例，但没有能力在一个不到30万字的小说里面写出一个世界；马尔克斯所写的拉丁美洲世界是最混乱的世界，所以他能够写出来，不是别人都写得出来。
+- **莫言在莎士比亚故居发誓是瞎扯**：余华澄清莫言在莎士比亚故居发誓要成为剧作家是瞎扯；莫言小说对话很精彩，20多年前就开始写话剧了，只是写了没拿出来；余华与苏童、莫言三人一起去莎士比亚故居，莫言在挑选帽子，帽子钱还是余华付的，买了三顶一模一样的深蓝色帽子，上面有莎士比亚名字，后来找不着了。
+## 对网络热度的看法
+- **走红后的冷静期**：余华因互联网走红后停了一年，任何活动、任何采访都不做；当时有节目联系他，他说抱歉，现在在一年的冷静期中间，因为按照过去的经验，只要一年在媒体上消失就马上过去了。
+- **自媒体时代的不同**：余华发现自媒体时代不是这样，会把几十年前的事情都翻出来，以前说过的话也给你翻出来；互联网上关于他说的话有一半不是他说的。
+- **不担心喜欢会消散**：余华不担心网红热度会消散，因为他的工作不是说话，是写作；可能今天因为一句话突然被人关注，又说错一句引发愤怒，过了十年以后又众人喜欢，但对他来说不说话也挺好。
+## 人生感悟与姿态
+- **第一次看到大海的感受**：余华童年第一次看到大海时，没有看到过如此宽阔辽阔的景象，感觉到一种宽阔的感觉，所以领悟到人生就是宽广的；小时候的人生感受是向前看的，现在是往后看的，回忆占多了。
+- **海流中游泳的经历**：余华讲述小时候每年夏天在海盐游泳，有一天发现自己进入海流，知道不能挣扎只能跟着走，一直到了40里外的平湖乍浦才爬上来，赤脚沿着海边走回来，天快亮了；刚开始紧张害怕以为要死在海里，后来放心，最后被海流带回家，那一刻真的感动了，觉得海浪带我回家了。
+- **三亚的星空与月光**：余华说在三亚看到了小时候的天空，因为这地方没有污染；晚上经常和太太走路看天空看月亮，月亮经常出现光晕，通过光晕发现月光是金色的，不是银色的。
+- **希望留下的姿态**：余华希望在历史长河中留下的姿态是遗忘的姿态；那些能够勉强被微风吹进耳朵的人，那也是勉强吹进来的，假如历史的长河里有一个主题，这个主题就是一个一个世界、一个一个的人。
+# 关键引语与金句
+&gt; “假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的，坐下来让屁股和椅子建立友谊，这是很重要的。”
+- 回应文学创作1.0阶段最重要的时刻是什么。
+&gt; “当时我觉得我将可能我的目标是对着那个托尔斯泰和陀思妥耶夫斯基去的，现在我知道我离他们的距离是不可逾越的。”
+- 谈到年轻时写作的野心与幻想。
+&gt; “我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。”
+- 谈到2006年开始写的一部长篇小说因感觉远去而搁置，感慨浪费了最好的写作时间。
+&gt; “把悲伤留给虚构，把欢乐留给现实。”
+- 谈到自己作品几乎都是悲剧，想先写完一个喜剧改变读者印象。
+&gt; “我能够走到的高度已经就是我现在的高度，我能够允许自己下滑一下，但再不要下滑得太多。”
+- 谈到不再追求高度，转而追求宽度。
+&gt; “我们整整一代中国作家都想在一本书里边写那个一个世纪的故事，但是其实没有必要。”
+- 谈到马尔克斯对一代中国作家的影响与反思。
+&gt; “现在在互联网上，起码我看到的我看到的啊，关于我的说的话，有一半不是我说的。”
+- 谈到自媒体时代被翻出旧事、被安上非本人说过的话。
+&gt; “假如那个历史的长河里边有一个主题的话，这个主题就是遗忘的姿态。”
+- 回应希望以什么样的姿态留在历史长河中。</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>11212/3761</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="13.5" customHeight="1" s="9">
       <c r="A38" s="6" t="inlineStr">
@@ -13464,6 +13892,84 @@
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次讲座为访谈式讲解，主讲人围绕柏林战役展开介绍，涵盖战役背景、双方兵力部署、战役过程、结局及影响，并解答听众关于城市作战、希特勒自杀、英美未攻柏林、影视书籍推荐等问题。战役背景方面，1945年苏军进抵奥德河-尼斯河一线，距柏林60公里；英美联军在易北河，距柏林100-120公里。苏军参战部队为白俄罗斯第一方面军（朱可夫元帅）和乌克兰第一方面军（科涅夫元帅），总计约250万人；德军防守部队包括中央集团军群残部、柏林卫戍部队及国民掷弹兵部队，总兵力约100万人。战役过程：1945年4月16日苏军炮轰德军阵地并越过奥德河、尼斯河；4月20日左右进抵柏林城区（潘科区及帕卡洛镇），4月24日突进市区；4月30日希特勒与妻子爱娃·布劳恩在地堡自杀，尸体被部下焚烧；4月30日夜间苏军占领国会大厦；5月2日柏林德军全部投降，战役结束；5月9日德国宣布无条件投降，二战欧洲部分正式结束。战役影响：奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直至1990年统一；日本于1945年9月2日在密苏里号军舰上签署无条件投降书，二战彻底结束。
+# 核心观点与论证
+## 战役背景与战略态势
+- **战役定位**：柏林战役是第二次世界大战欧洲战场的最后一次大规模战斗，也是苏德战争期间苏联和德国进行的最后一场大规模战役。
+- **苏军先机**：1945年苏军已进抵奥德河、尼斯河一线（今德国和波兰边境地区），距离柏林仅60公里；英美联军才到达易北河一带，距离柏林100–120公里，苏联获得先发制人机会。
+- **苏军部署**：白俄罗斯第一方面军（指挥官朱可夫元帅）从奥德河—法兰克福方向北部对柏林突击与包围；乌克兰第一方面军（指挥官科涅夫元帅）由克拉科夫及德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。
+- **德军兵力**：防守部队为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（由年纪较大的老人和16岁以下孩子组成的民兵），总兵力约100万人，从柏林到桑多梅日桥头堡及奥德河一带布防。
+- **苏军兵力**：白俄罗斯第一方面军和乌克兰第一方面军总计约250万人，从北部什切青到南部德累斯顿形成合围网。
+## 战役进程与关键节点
+- **第一阶段**：1945年4月16日，苏军以数以千计的火炮和卡秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击。
+- **推进受阻**：因德军在桑多梅日桥头堡修筑防线，苏军拖至4月20日左右才进抵柏林城区（今柏林潘科区及帕卡洛镇一带），4月24日白俄罗斯第一方面军突进柏林市区，科涅夫部队仍在向柏林边缘靠近。
+- **德军抵抗**：德军温克第十二集团军与苏军一直周旋，是战役中表现突出的部队之一。
+- **希特勒之死**：4月29日希特勒与情妇爱娃·布劳恩举行婚礼；4月30日，柏林已被苏军围死、苏军距其地堡仅两条街，希特勒不甘被俘，与爱娃·布劳恩一起饮弹自尽。
+- **战役结束**：4月30日夜间苏军占领德国国会大厦；5月2日经谈判拉扯，柏林城防司令魏德林宣布柏林其余地区德军向苏军缴械投降，柏林战役结束；5月9日德国宣布无条件投降，二战欧洲部分正式结束。
+## 城市作战特点
+- **定义与危险**：城市作战中敌人可能从任何方向攻击，坦克和车辆在街道上易受攻击，敌人可从建筑物或其他街道用火箭筒和机枪攻击，非常困难且危险。
+## 英美未攻柏林的原因
+- **战后协议**：盟国事先已就战后德国地盘划分达成协议，柏林战后属于苏联，但会分出一半区域给西方盟国（即后来的西柏林）。
+- **艾森豪威尔考量**：美军统帅艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后仍需撤出，得不偿失。
+- **战略取舍**：西方盟军更倾向占领德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等；且打完德国后盟军还有求于苏联协助对日作战。
+## 战役细节与影响
+- **易北河会师**：西欧部队与东边苏联部队事先没有交流，在易北河会师只是偶然，双方见到对方部队才知道合拢，高层未达成共识。
+- **红旗插国会大厦**：著名的「红旗插上国会大厦」照片中，红旗并非标准苏军制式军旗，而是士兵临时用床单和颜料绘制；插旗士兵手上戴有三块从德国老百姓抢来的手表，摄影师为国际观瞻要求重新摆拍。
+- **战后格局**：柏林战役奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直至1990年两个德国才统一。
+- **二战终结**：日本于1945年9月2日在密苏里号军舰上签署无条件投降书，第二次世界大战彻底结束。
+# 金句总结
+&gt; 谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。
+- 背景：讲到柏林战役对苏联的战略意义时，强调占领柏林在战后国际格局中的象征性价值。
+&gt; 此时对于纳粹德国来说可以说是丧钟敲响的开始。
+- 背景：讲到苏军已进抵奥德河—尼斯河一线、距柏林仅60公里时，对德军处境的判断。
+&gt; 城市作战……敌人可能从任何方向攻击，坦克和车辆在街道上易受攻击，非常危险。
+- 背景：回答主持人关于城市作战与野外作战区别的提问时，用英文简要描述城市作战的危险性。
+&gt; 希特勒不甘于在兵败之后被苏联俘虏，所以说他举枪自尽了。
+- 背景：回答听众关于希特勒是否自杀的提问时，说明其自杀动机。
+&gt; 大部分人都坚信纳粹没有覆灭，还在就是以自欺欺人的方式麻痹自己和苏军进行的就是不同程度的战斗。
+- 背景：解释希特勒尸体被焚烧、遗体下落不明导致外界谣言盛行时，指出当时德军内部的自欺欺人心态。
+&gt; 与其这样，还不如说是尽可能去占领更多德国的精华地带……柏林就让给苏联吧。
+- 背景：回答英美为何不攻打柏林时，转述艾森豪威尔的战略考量——占领柏林得不偿失，不如占领慕尼黑、斯图加特等德国精华地带。
+&gt; 那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜。
+- 背景：补充听众提到的易北河会师细节时，说明红旗插上国会大厦著名照片中旗帜的临时制作背景。
+&gt; 奠定了冷战欧洲部分的一个基调。
+- 背景：回答柏林战役胜利后的世界格局时，指出战役对德国分裂为东西两个德国、冷战欧洲格局形成的深远影响。
+# Q&amp;A 环节
+**听众**：城市作战跟野外作战有什么明显区别或定义吗？
+**主讲人**：城市作战中敌人可能从任何方向攻击你，你的坦克和车辆就在街道上，敌人可以从建筑物或其他街道用火箭筒和机枪攻击你的部队，所以非常困难和危险。
+**听众**：是不是这个战役里面希特勒自杀了？
+**主讲人**：是的。1945年4月30日，柏林已被苏军围死，苏联红军距离希特勒所在的地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，于是举枪自尽，和他的夫人爱娃·布劳恩一起。
+**听众**：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么受关注？
+**主讲人**：因为他自尽后，部下用汽油把他的尸体焚烧了，到今天为止没有见到他遗体的全貌，只获得一堆烧焦的焦炭，所以外界说法不一，没有确切证据。除了少数亲信外，大部分人坚信纳粹没有覆灭，以自欺欺人的方式麻痹自己继续战斗，各种流传民间的说法褒贬不一，导致谣言盛行。
+**听众**：想更详细了解这个战役，有什么影视推荐吗？有拍成影视吗？
+**主讲人**：苏联有他拍的《柏林战役》，德国有《帝国的毁灭》。
+**听众**：那他们的细节或倾向有什么不同？
+**主讲人**：德国角度更多是希特勒最后生平以及他关于柏林防守的人事任命；苏联方面更多强调从高层到基层的各方面描写，高层的运筹帷幄以及基层官兵的舍生忘死。
+**听众**：主要进攻柏林的是苏联方面的部队吗？
+**主讲人**：是的，同时半数的还有波兰共产党的部队。
+**听众**：那为什么英美不打柏林呢？
+**主讲人**：丘吉尔当时想抢占柏林，但盟国事先已就战后德国地盘划分达成协议，柏林战后属于苏联，会分出一半区域给西方盟国（即后来的西柏林）。美军统帅艾森豪威尔认为攻占柏林会增加不必要伤亡，且占领后还要撤出，得不偿失，不如尽可能占领德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等。而且打完德国后盟军还有求于苏联一起对日作战。
+**听众**：这场战役大概持续了多久？
+**主讲人**：从4月16日开始，一直进行到5月2日。
+**听众**：有什么书可以看的吗？
+**主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记里关于柏林战役后苏俄和西方博弈的内容，涉及西柏林地区划分和德国边境重新划定。
+**听众**：当时柏林战役胜利之后，世界形成了怎样的格局？
+**主讲人**：奠定了冷战欧洲部分的基调，德国后来分裂成东西两个德国，边界大致沿今天的罗斯托克到南部图林根一带形成，此后一直到1990年两个德国才统一。
+**听众**：B站上比较火的鬼畜片段就是这个战役末期发生的吗？
+**主讲人**：对，那个希特勒鬼畜片段出自电影《帝国的毁灭》，尤其是他大骂温克丢下柏林逃跑那一段。</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4609/3773</t>
         </is>
       </c>
     </row>
@@ -13609,6 +14115,63 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t># 全文摘要
+会议为多人自由讨论，共5位发言人参与，围绕社会规则合理性、理想工作形态、AI与机器人未来及语音分离标注测试等话题展开。讨论认为必须买房、结婚等规则不合理，工作应基于兴趣而非与金钱挂钩；理想工作形态方面，有观点认为应让AI承担苦活累活，而非从事创作艺术。关于机器人意识与人类未来，存在机器人可能罢工、反抗并奴役人类的担忧，也有观点认为机器人只需执行命令、不必有思想。会议以分享为主，未形成明确结论。
+# 分段速览
+## 00:00:02-00:01:40 社会规则合理性讨论
+发言人1提出必须买房、必须结婚等社会规则不合理，经济不好时更不可行；发言人2补充必须结婚生子，并认为结婚、买房、升职都取决于遇到的人和自身经济能力，不能说得太绝对；发言人3认为历史对静辉来说都是合理的，并指出人必须工作是合理的。发言人1进一步表示，人不工作不产生财富世界无法运转，工作本身可能合理，但应做自己想做的事，不应与金钱挂钩。
+## 00:01:40-00:04:13 理想工作形态与AI替代劳动
+发言人2询问大家理想中的工作状态，发言人1表示每天按兴趣干活最好；发言人4提出不干活更好的可能性；发言人3举例宠物博主工作轻松，发宠物视频剪视频即可赚钱，发言人2补充游戏高手也可行。发言人1指出总有些脏活累活没人愿意承担，发言人3认为应让AI做苦活累活而非创作艺术。发言人2引用蔡明小品中机器人反叛情节，讨论机器人替代劳动后人类幸福感是否提升，发言人1认为机器人负责生产、人负责享受虽好但规则难以实现，并提到上层可能不愿让平民过得太好、存在阶级优势。
+## 00:04:13-00:08:05 机器人意识与人类未来
+发言人5提到扫地机器人未来可发展为在家打扫做饭的机器人，发言人1认为以后养老靠自己。发言人2担忧机器人有独立思想意识后可能罢工、反抗并奴役人类，类似《终结者》剧情；发言人3提到斯皮尔伯格人工智能电影也是类似结局，并认为智能和思想可能无法分开；发言人5认为机器人只需接受命令执行命令，不必有思想，但思想可能带来不良影响。发言人2列举军队单兵装甲外骨骼、智能枪械、排雷机械狗等半机械人应用，并引用游戏《重返德军总部》超级战士和数码宝贝中机械邪龙兽等例子。
+## 00:08:05-00:10:56 动漫举例与语音分离测试
+发言人2详细讲述数码宝贝中安多路兽被黑色魔轮控制后仍能通过人脸识别判断身份的情节，认为九几年日本人已有此构想，并提到机械邪龙兽是精密超级计算机形成的生命体；发言人4询问具体出处，发言人2确认是第一二部内容。发言人3提醒时间，随后提出测试两人同时说话时的语音分离，发言人1认为标注的人需要认识他们的声音，并认为单人麦克风很强，最后结束会议。
+# 要点梳理
+## 社会规则合理性讨论
+- **发言人1**：必须买房、必须结婚等规则不合理，经济好的时候可以，经济不好的时候不太可以。
+- **发言人2**：必须结婚生子也是不合理规则；结婚、买房、升职都取决于遇到什么样的人及自身经济能力，不能说得太绝对。
+- **发言人3**：人必须工作是合理的。
+- **发言人1**：工作合理，但应做自己想做的，不要与金钱挂钩太紧密。
+## 理想工作形态与AI替代劳动
+- **发言人2**：询问大家理想状态中的工作是什么样的。
+- **发言人1**：理想工作是每天起来想干啥就干啥，按自己兴趣干活。
+- **发言人4**：提出有没有可能不干活更好。
+- **发言人3**：举例宠物博主工作好，每天发宠物日常、剪剪视频就能赚钱。
+- **发言人2**：补充游戏高手也是理想工作。
+- **发言人1**：指出总有些脏活累活大家都不想干，没人承担。
+- **发言人2**：提出以后机器人问世可以承担苦活累活。
+- **发言人3**：认为应让AI做苦活累活，而不是让它搞创作、艺术。
+- **发言人2**：引用蔡明小品情节——机器人被敲脑袋后反叛，把牛皮制品手表和皮鞋煮成牛肉汤。
+- **发言人1**：认为机器人负责生产、人负责享受挺好，但质疑这种规则能否实现。
+- **发言人2**：认为AI普及并普惠到实体后，若机器人有了自己的思维，只要人类控制得当，人类或可不用干苦活累活。
+- **发言人1**：认为上层的人不想让平民过得太好，要保持对普通民众的优势，存在阶级问题。
+## 机器人意识与人类未来
+- **发言人2**：担忧机器人有独立思想意识后不受人类控制、搞罢工、反向控制人类，类似《终结者》剧情，人类成为机器人奴隶。
+- **发言人3**：提到斯皮尔伯格《人工智能》电影也是类似结局；认为机器人会不会把自己当成被压迫对象是哲学问题。
+- **发言人5**：认为机器人只要能接受到命令、执行命令就行，不必有思想。
+- **发言人3**：认为机器人得有智能，但智能和思想可能没法分开。
+- **发言人5**：指出思想可能带来不好影响，如让它往前走它去前面打了人。
+- **发言人2**：认为机器人可能成为犯罪代理人、职业杀手或超级战士，独立意识群体罢工后反抗人类，后果灾难性。
+- **发言人2**：列举军队已有单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人状态，排雷机械狗和机械车已在用。
+- **发言人2**：举例游戏《重返德军总部》超级战士、数码宝贝中守卫兽和机械装甲兽进化成安多路兽、机械邪龙兽（精密机械式超级计算机形成生命体，专为破坏而存在）。
+- **发言人2**：提到数码宝贝第二部第七集安多路兽被黑色魔轮控制后仍能通过人脸识别判断人，主角嘉儿通过记忆唤醒其最终记忆，称该集让自己最早有了人脸识别和人工智能识别的概念。
+## 语音分离标注测试
+- **发言人3**：提出测试两人同时说话时的语音分离。
+- **发言人1**：认为标注的人需要认识他们的声音；认为单人的麦很强，应该能分离单人声音。
+- **发言人5**：提及身高比较（语音识别相关讨论，原文表述不完整）。
+- **发言人3**：宣布会议结束。</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3931/2477</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="13.5" customHeight="1" s="9">
       <c r="A40" s="6" t="inlineStr">
@@ -13696,6 +14259,55 @@
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t># 全文摘要
+会议为两人参与的闲聊式讨论，由发言人1主导、发言人2补充提问，围绕哥斯拉系列电影剧情展开，并延伸至核废水排放的现实影响。讨论覆盖哥斯拉系列历史与日美版本剧情、角色设定、核废水主题及切尔诺贝利事件对比等板块。哥斯拉首部电影诞生于1954年，起源为海底生物吸食核废料后变异，在日本神话中是大自然的守护神；美国版《哥斯拉大战金刚》中机械基多拉最终被金刚和哥斯拉联手击败，日本版《新哥斯拉》（2016年）中哥斯拉被无人机投放炸弹耗尽能量后以冷冻剂封印。讨论以分享为主，未形成明确结论。
+# 分段速览
+## 00:00:00-00:09:48 哥斯拉系列电影剧情讨论
+发言人1开场介绍哥斯拉系列电影背景，指出首部电影诞生于1954年，迄今约70多年，日美两国翻拍多个版本。哥斯拉起源为海底生物吸食核废料后变异，在日本神话中是大自然的守护神，因人类频繁核试验破坏生态而报复人类。发言人1梳理美国版剧情线：2014年新版中哥斯拉与人类携手团灭以核废料为能源的雾托物种；第二部《怪兽之王》中人类核试验唤醒沉睡怪兽，基多拉降临，人类试图用水下爆炸让哥斯拉窒息，反被基多拉干扰，最终人类用核废料唤醒哥斯拉击败基多拉；第三部《哥斯拉大战金刚》中反派残余势力将基多拉残骸加装机械装甲制成机械基多拉，金刚与哥斯拉联手将其击败。发言人1还介绍日本版剧情，包括2016年《新哥斯拉》中哥斯拉吸收核废料不断升级，最终被无人机投放炸弹耗尽能量、以冷冻剂封印，以及2004年《哥斯拉最后的战斗》有章子怡参演。讨论中提及哥斯拉与奥特曼同属圆谷英二作品但为不同时间线，哥斯拉为地球本土物种，奥特曼来自奥特之星。
+## 00:09:48-00:15:17 核废水排放的现实影响与切尔诺贝利对比
+讨论由哥斯拉的核废水主题延伸至现实核废水排放问题。发言人2提到在日本留学期间，因日本开始排放核废水，购买中国进口的鱼，并指出日本产品因国产标签而价格昂贵。发言人1表示即使不吃海产品，日常饮水也可能受影响，并询问核废水对身体的伤害，但未获明确回答。发言人1指出目前未出现类似哥斯拉的变异案例，但存在白血病等病变，切尔诺贝利地区生物出现畸形但未变强。发言人1对比切尔诺贝利事件，指出核反应堆已被水泥封存，周边成为无人区，认为比日本排放核废水更负责任。发言人2提及《使命召唤4》游戏中切尔诺贝利关卡，车臣叛军试图挖掘核废料，被英国SAS特种部队主角狙杀未遂。
+# 要点梳理
+## 哥斯拉系列电影剧情讨论
+- **首部电影**：1954年诞生，迄今约70多年，日美翻拍多个版本。
+- **哥斯拉起源**：海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
+- **神话定位**：在日本神话中是大自然的守护神，攻击人类源于人类无限制搞核试验、破坏自然生态。
+- **扩展题材**：人类频繁战争和核试验唤醒沉睡生物、招致外星生物入侵；也有哥斯拉作为守护神与人类携手打败其他怪兽和外星生物的设定。
+- **《哥斯拉怪兽之王》**：反派基多拉为外星生物，是龙头老大角色。
+- **《哥斯拉大战金刚》**：基多拉被哥斯拉打败后，人类反派势力将基多拉仅存的一个脑袋加装机械装甲复合升级为机械基多拉，差点打败哥斯拉；金刚挺身而出，与哥斯拉不计前嫌联手击败机械基多拉，战斗地点在香港九龙。
+- **摩斯拉**：日本神话中的蝴蝶，负责给哥斯拉疗伤。
+- **哥斯拉正反派形象**：既有作为反派出现的印象，也有作为正面形象出现的情况；基多拉降临地球时哥斯拉与人类携手对抗。
+- **2004年日本电影《哥斯拉最后的战斗》**：有中国演员章子怡参演。
+- **续集机制**：哥斯拉每次都没被真正杀死消灭，重新沉睡后形成不同版本的续集。
+- **金刚与哥斯拉冲突起因**：金刚领地为热带雨林，哥斯拉领地为海洋，海洋淹没热带雨林后双方因地盘起冲突。
+- **美国版2014年第一部**：另外两个物种（蝙蝠类）以核弹、核废料为能源食物，哥斯拉为维护地球安全与人类携手团灭该物种（名为雾托）。
+- **美国版第二部**：人类频繁核武器实验唤醒全球沉睡怪兽，基多拉降临地球；人类试图用水下子母弹和核试验方式让哥斯拉在水里窒息死亡，但基多拉为外星物种、武器对其无效，哥斯拉差点被溺死；人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉。
+- **福原博士**：曾表示不能用核办法对付基多拉，因基多拉是外星生物；人类差点成猪队友，基多拉没事、哥斯拉差点被误杀。
+- **日本版剧情**：最早哥斯拉作为怪兽出场；翻拍剧情与美国版类似，但人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀外星人控制的怪兽、解放地球。
+- **《新哥斯拉》（2016年日本版）**：海里蜥蜴类生物喝核废水后不断壮大，吸收核废料后升级变大；人类各种武器攻击不仅无效反而增强其战斗力和战斗形态；最终以无人机投放炸弹耗尽能量，再用冷冻剂封印。
+- **哥斯拉与奥特曼关系**：导演最早都是圆谷英二，但属于不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正面形象，未直接战斗过。
+- **拉顿**：会飞的翼龙/鸟，在奥特曼和哥斯拉不同作品中分别与正派形象战斗过。
+- **哥斯拉系列作品清单**：哥斯拉大战人类、哥斯拉大战机械哥斯拉、哥斯拉大战基多拉、哥斯拉最后的战斗、新哥斯拉、2014年新版本哥斯拉的复活、哥斯拉怪兽之王、哥斯拉大战金刚。
+- **题材延续原因**：只要日本不停止排放核废水行为，此类题材不会停。
+## 核废水排放的现实影响与切尔诺贝利对比
+- **日本核废水排放**：发言人1指出万一有病变生物变异说不清楚；此前不让进口日本产品，现已放开。
+- **发言人2留学经历**：在日本留学期间日本开始排放核废水，当时吃的鱼都买国内（中国）进口的。
+- **健康影响**：发言人1表示喝了核废水对身体损耗的伤害没人说得准，目前没看到变异案例，但肯定有得各种白血病等病变；不会像哥斯拉那样喝了核废料马上变异成庞然大物。
+- **日本国产产品价格**：发言人2称日本有迷之民族自信，产品打上国产标签就非常贵，虽然东西并不怎么样。
+- **切尔诺贝利事件**：核反应堆被水泥盖住封存，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里是无人区；发言人1认为相比日本，切尔诺贝利至少拦截封存了，比日本核废水处理更负责任。
+- **切尔诺贝利生物变异**：有生物长得奇怪、变畸形，但没说变强。
+- **相关文艺作品**：有电视剧、电影和游戏涉及切尔诺贝利；《使命召唤4》双狙人关卡中，车臣派军去切尔诺贝利挖核废料，被英国SAS特种部队主角狙杀，未狙杀成功、打断一条胳膊。</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5319/2763</t>
         </is>
       </c>
     </row>
@@ -13931,6 +14543,81 @@
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为6位成员（发言人1至发言人6）围绕“18岁以前的深刻印象和记忆”展开的分享型讨论，由发言人1发起，引导大家回忆逃课、网吧游戏、追星、乐队等经历。成员依次分享了初中走读时每周一下午4点放学后聚集游戏厅网吧的经历，高中因高考压力不敢逃课转而追星、搞乐队，以及各自喜爱的小说、漫画、杂志与电脑游戏。议题范围涵盖逃课与游戏经历、小说漫画与杂志、电脑游戏与游戏鄙视链、第一人称射击游戏与暴力内容、求生之路与生化危机等游戏剧情、游戏与电影的关系、塔防游戏与使命召唤等。讨论以分享观点为主，未形成统一结论，整体按话题自然流转、漫谈发散推进，由发言人1多次引导转向新议题。
+# 发言要点
+## 18岁前的逃课与游戏经历
+- **发言人1**：初中走读，每周一下午4点放学后去游戏厅、网吧，流行玩穿越火线（CF）、反恐精英online（CS online）、使命召唤、战地、魔兽等游戏。
+- **发言人1**：高中因高考压力不敢逃课，主要追星和搞乐队，喜欢朋克金属音乐，涉及架子鼓、电吉他、贝斯。
+- **发言人2**：18岁之前没逃过课，大学后逃过一次课。
+- **发言人3**：逃课是正常现象。
+- **发言人4**：上大学后就不算了。
+## 小说、漫画与杂志
+- **发言人5**：特别喜欢郭敬明的小说。
+- **发言人2**：看郭敬明小说觉得难受、扭曲，提到《梦里花落知多少》。
+- **发言人4**：班上特别流行看柯南。
+- **发言人1**：流行看名侦探柯南和香港漫画《老夫子》。
+- **发言人5**：提到《萌化三国》。
+- **发言人2**：提到《意林》《读者》《故事会》等杂志，称《意林》当时讲得好，现在反转了。
+## 电脑游戏与游戏鄙视链
+- **发言人4**：提到摩尔庄园、赛尔号。
+- **发言人2**：提到穿越火线、地下城与勇士。
+- **发言人1**：初中流行单机游戏求生之路，联机局域玩。
+- **发言人5**：玩过仙剑四，也玩过仙剑或古剑系列。
+- **发言人2**：初中玩魔兽争霸（单机），与魔兽世界（网游）有区别。
+- **发言人5**：提到英雄联盟、DOTA、王者荣耀，并问是否有鄙视链。
+- **发言人2**：认为王者荣耀在鄙视链最低端。
+## 第一人称射击游戏与暴力内容
+- **发言人1**：因在贴吧和QQ空间写文章骂穿越火线，被穿越火线平台封禁，后成为CS反恐精英铁杆粉丝。
+- **发言人1**：喜欢CS僵尸模式，被舞蹈队说跳舞姿势像舞体僵尸。
+- **发言人5**：质疑游戏暴力且无年龄限制，称感觉是姑父、叔叔那辈人玩的游戏。
+- **发言人1**：求生之路第二部血腥暴力，能用东洋刀、电锯、砍刀砍丧尸群，砍飞脑袋四肢、血喷一脸，因此Steam要求18岁以上才能注册账号。
+- **发言人2**：称穿越火线现在看起来像像素游戏。
+## 求生之路与生化危机等游戏剧情
+- **发言人1**：认为求生之路制作团队精准预测美国政府在大灾难中的表现，2020年新冠疫情爆发后游戏重新火爆。
+- **发言人1**：讲述求生之路剧情：美国政府默不作声导致病毒失控，军队暴力清理但被感染，主角团不信政府承诺、自己拿起枪自救。
+- **发言人1**：主角团是无症状感染者，从僵尸角度看是异类；病毒类似狂犬病的狂暴病毒感染。
+- **发言人2**：欧美玩家爱玩打僵尸游戏，模式一上线欧洲玩家疯狂在线。
+- **发言人1**：生化危机也是病毒泄露、政府反应迟钝不作为，生化三用核武器把整个城市夷平。
+- **发言人2**：生化危机不敢玩，挺恐怖。
+- **发言人5**：过年与表姐表弟看恐怖片，大家都跑了。
+## 游戏与电影的关系
+- **发言人2**：问游戏和电影谁先谁后。
+- **发言人1**：生化危机先有游戏后有电影；求生之路是在惊变48小时、生化危机基础上，先有电影后有的游戏。
+- **发言人4**：问变形金刚先有玩具还是电影。
+- **发言人1**：变形金刚先有玩具，绿日乐队（Green Day）出过介绍变形金刚的MV。
+## 塔防游戏与使命召唤
+- **发言人3**：小时候常玩塔防游戏，如植物大战僵尸，现在还在玩。
+- **发言人2**：植物大战僵尸有特别变态的版本，后期满屏子弹，电脑都卡得扛不住。
+- **发言人1**：使命召唤黑色行动基于冷战时期美苏真实历史；现代战争虚构，后期剧情美国挑衅俄罗斯、俄罗斯反杀到美国本土，结合当前俄军在乌克兰表现，有点高估俄罗斯。
+- **发言人2**：称使命召唤这类游戏太男性化。
+# 共识形成
+- **一致意见**：与会者普遍认同18岁前逃课、网吧游戏、追星、看小说漫画等是共同的时代记忆；对游戏与电影关系形成共识——**生化危机先有游戏后有电影**，求生之路是在《惊变48小时》《生化危机》基础上先有电影后有的游戏，变形金刚先有玩具。
+- **倾向性认识**：多数人认为游戏存在鄙视链，发言人2认为王者荣耀处于鄙视链最低端；发言人1认为《求生之路》制作团队精准预测了美国政府在大灾难中的表现，2020年新冠疫情后该游戏重新火爆。
+- **主要分歧点**：发言人1与发言人5在游戏暴力与年龄限制问题上看法不一致——发言人5质疑此类游戏暴力且无年龄限制，发言人1解释《求生之路》第二部血腥暴力，导致Steam要求18岁以上才能注册账号；发言人2认为《使命召唤》等游戏太男性化，发言人1则详细介绍其剧情设定。
+# 待探讨问题与后续
+- **未确认**：发言人5质疑穿越火线、求生之路等游戏暴力且无年龄限制，发言人1解释求生之路第二部因血腥暴力导致Steam要求18岁以上才能注册账号，但未确认该年龄限制的具体实施时间与执行方式。
+- **未确认**：发言人2提到《意林》内容「现在怎么都反转了」，未展开具体指哪些内容反转，话题被搁置。
+- **未确认**：发言人5提到《萌化三国》，未说明其内容或来源，其他成员未回应。
+- **未确认**：发言人1提到自己因在贴吧和QQ空间写文章骂穿越火线被平台封禁，未说明封禁的具体时间、平台规则依据及封禁时长。
+- **未确认**：发言人1认为《求生之路》制作团队精准预测美国政府在大灾难中的表现，2020年新冠疫情后游戏重新火爆，该判断属个人观点，未获其他成员验证或讨论。
+- **未确认**：发言人1提到《使命召唤：现代战争》后期剧情「高估俄罗斯」，结合当前俄乌冲突表现，未展开具体剧情对照分析。
+- **未确认**：发言人2提到植物大战僵尸有「特别变态的版」，后期满屏子弹导致电脑卡顿，未说明该版本名称或获取渠道。
+- **未确认**：发言人4提到班上流行看「柯洁男」，发言人1纠正为《名侦探柯南》，未确认该口误是否影响后续讨论。
+- **未确认**：发言人1提到《变形金刚》「有点抄袭小日本的当时的一些个题材」，未展开具体抄袭对象或依据。
+- **未确认**：发言人2提到欧美玩家「整个欧洲年轻人都在打僵尸」，未提供数据来源或具体游戏名称。</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6453/2902</t>
         </is>
       </c>
     </row>
@@ -14200,6 +14887,67 @@
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为一场围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说的自由讨论，由发言人1、发言人2、发言人3、发言人4四人参与，以漫谈分享为主，未形成统一结论。讨论由发言人1提议继续此前未完成的《红楼梦》话题开场，随后自然延伸至《金瓶梅》与《水浒传》的对比、《西游记》中佛教虚伪的描写，以及各书历史背景的辨析。议题范围涵盖《红楼梦》的官场暗线与四大家族兴衰、薛宝钗结局版本争议、冷香丸与吃螃蟹等生活细节描写；《金瓶梅》中武松报仇未成与西门庆的逃脱、西门庆妻妾群像及小人物发展史主题；《西游记》中如来佛祖收300两黄金、寺院住持贪袈裟自焚等情节；以及《红楼梦》无明确朝代、映射曹雪芹经历、《金瓶梅》与《水浒传》同属北宋时期等历史背景问题。讨论整体呈漫谈发散式推进，各议题间自然过渡，发言人多以补充细节、提出疑问或分享印象的方式参与，未就任何议题达成明确结论。
+# 发言要点
+## 《红楼梦》讨论
+- **发言人3**：《红楼梦》有一条官场暗线，即朝堂政权变化；四大家族兴衰与官场地位相关，王熙凤前期地位高、结局惨，与其兄长的官场地位及先死直接相关。
+- **发言人4**：质疑四大家族「感觉就没几个人」，每家就两家人多一点，王熙凤家、史家、薛宝钗家都只见典型人物，看不出「很牛逼」的家族规模。
+- **发言人1**：背诵四大家族诗句——「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」。
+- **发言人3**：四大家族整体都在走下坡路，对应王朝家族的衰败。
+- **发言人4**：小时候看《红楼梦》没看明白，但对吃螃蟹的讲究印象深刻——江南吃螃蟹要卸钳、卸身，第一次知道吃螃蟹需要这么多工具。
+- **发言人3**：冷香丸的配方讲究节气——要雨水那一日的雨水、小雪那一日的雪，每个节气都要正好碰上；花要用春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
+- **发言人3**：薛宝钗结局有版本争议——120回版本中她嫁给贾宝玉，但贾宝玉不久出家，好多人说是无性婚姻；另看过的版本说她后来怀了一个孩子。
+- **发言人2**：追问「那是贾宝玉的还是」；**发言人3**回应那是狗血版本；**发言人1**认为「这个应该不至于弄这么狗血」。
+- **发言人4**：《红楼梦》很明显在映射当时时代，有说法称演的是曹雪芹的经历——他以前好像是个大家族。
+- **发言人3**：要不然他写不出那么多细节。
+- **发言人1**：《红楼梦》当时是禁书，已经不敢写明朝代，说朝代更禁。
+## 《金瓶梅》与《水浒传》讨论
+- **发言人1**：金瓶梅从武松杀武大郎之后开始写；武松去找西门庆报仇时，西门庆在楼上喝茶，仆人报信后从楼上翻下去逃脱——原水浒传里没有翻下去、直接砍头，金瓶梅里翻下去就给了他一线生机。
+- **发言人1**：之后武松怎么都报不了仇，被发配，故事转向西门庆线；武松报仇被高官、大家族权势打压下来，所以很真实。
+- **发言人3**：金瓶梅是西门庆这个小人物的发展史，写他一个无赖如何爬到比较高、过得比较舒服，官场如何黑。
+- **发言人2**：询问西门庆后来和宋江等人有没有交集；**发言人3**认为应该不会写，但丞相是同一个。
+- **发言人4**：西门庆最后跟童贯还是谁，跟中央攀上线，当地一霸。
+- **发言人2**：询问西门庆结局在两个版本中的差异——水浒里脑袋被砍下来；**发言人3**回应金瓶梅版本里西门庆是纵欲过度死。
+- **发言人3**：西门庆有十个老婆，有的老婆特别懦弱，潘金莲属于很有心机、比较强势的那一种。
+- **发言人3**：西门庆一个老婆生病后去看和尚、不去治病，信迷信回来死了；金瓶梅里佛教也很黑，收灯油钱。
+- **发言人4**：金瓶梅比红楼梦接地气一点，也能学到东西。
+## 《西游记》及其他讨论
+- **发言人1**：西游记里如来佛祖说「区区收了300两黄金」——天庭派人帮一个国家，帮完回来如来嫌收得少。
+- **发言人2**：西游记里佛教虚伪的例子——孙悟空和唐僧单独取经时寄宿寺院，住持有很多袈裟，觊觎唐僧袈裟，后来引火把自己烧死了。
+- **发言人3**：红楼梦没有明确朝代，是一个写得很虚的故事；作者是那个时代的人，映射那个时代。
+- **发言人2**：水浒和金瓶梅是北宋时期，与红楼梦不同；三国、水浒都有明确历史人物和时间线，与真实事件大致相同。
+- **发言人2**：提到孙权二宫之争——太子孙登、鲁王孙霸之争，不同大臣支持不同儿子；孙权老婆王夫人有心机，和女儿孙鲁班一起反杀，把东吴政局搅得一团糟。
+# 共识形成
+- **一致意见**：与会者普遍认可《红楼梦》存在官场暗线，四大家族兴衰与官场地位相关，如王熙凤地位与其兄长官场地位相关；同时认可《金瓶梅》是西门庆这个小人物的发展史，武松报仇未成、被权势打压是故事转向西门庆的关键节点。
+- **倾向性认识**：多数人倾向认为《红楼梦》映射当时时代，有说法称是曹雪芹个人经历，发言人3补充「要不然他写不出来那个那么多的细节」；发言人1提到《红楼梦》当时是禁书，不敢写明朝代。
+- **主要分歧点**：发言人4质疑四大家族人数少，「每家就两家人多一点」，与诗句中「都很牛逼」的形容不符，发言人3未直接回应人数问题，仅以「整体都在走一个下坡路」解释；关于薛宝钗结局，发言人3提到120回版本中她嫁给贾宝玉但贾宝玉出家，有说法称无性婚姻，另有版本称她后来怀孕，发言人1认为「这个应该不至于弄这么狗血」。
+- **关键口径**：发言人1背诵四大家族诗句「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」；发言人1提到《西游记》中如来佛祖说「区区收了300两黄金」。
+# 待探讨问题与后续
+- **未确认**：《红楼梦》中四大家族是否真的只有少数人，发言人4质疑每家仅两家人多一点，发言人3回应称可能是没看书，书里人可能不少。
+- **未定论**：《金瓶梅》中西门庆的结局在不同版本中是否不同，发言人2询问水浒版与金瓶梅版结局差异，发言人3称金瓶梅版中西门庆是纵欲过度而死，水浒版中则是被武松砍头。
+- **未确认**：《红楼梦》是否映射曹雪芹个人经历，发言人4提到有这种说法，发言人3认为若非亲身经历写不出那么多细节。
+- **待核实**：《金瓶梅》中武松报仇线是否成功，发言人1讲述武松报仇被高官权势打压、被发配，发言人4询问武松报仇线是否存在，发言人3确认有报仇线但未成功。
+- **未确认**：《金瓶梅》中潘金莲在西门庆妻妾中的地位，发言人3称西门庆有约十个老婆，潘金莲属于有心机、强势的类型，发言人4询问潘金莲是否属于强势类型，发言人3表示印象中如此。
+- **待核实**：《金瓶梅》中西门庆一个老婆因迷信和尚而病死的情节，发言人3提及该细节，发言人4表示细节记不清。
+- **未确认**：《西游记》中如来佛祖收300两黄金的章节出处，发言人1提及该情节但忘记具体章节，发言人2询问后未得到明确答复。
+- **待核实**：《西游记》中寺院住持贪唐僧袈裟引火自焚的情节，发言人2提及但表示记不清细节，发言人3推测可能看的是电视剧版本。
+- **未确认**：《红楼梦》中薛宝钗的结局版本，发言人3提到120回版本中她嫁给贾宝玉但贾宝玉出家，有说法称无性婚姻，另有版本称她后来怀孕，发言人2询问孩子是否为贾宝玉的，发言人3称那是狗血版本。
+- **未定论**：《金瓶梅》与《水浒传》的关系，发言人2询问西门庆与宋江是否有交集，发言人3认为应该不会写但丞相是同一个；发言人2询问宋江起义是否成功，未获明确回答。
+- **未确认**：《红楼梦》的历史背景，发言人3称其没有明确朝代、是虚构故事，发言人4认为作者是那个时代的人、映射当时时代，发言人1提到《红楼梦》当时是禁书、不敢写明朝代。
+- **待核实**：东吴二宫之争中王夫人与孙鲁班搅乱政局的说法，发言人2提及该历史事件并询问大家了解程度，未获回应。</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5893/3343</t>
         </is>
       </c>
     </row>
@@ -14483,6 +15231,53 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t># 全文摘要
+会议为多人自由闲聊，参与者共六位发言人，未明确机构与主办方。前半段围绕个人阅读与综艺观看展开，发言人1提到反复阅读《红楼梦》多次，发言人2与发言人4表示不怎么看小说、更常看短剧和综艺；随后讨论《种地吧》与《克拉克森的农场》两部种地综艺，并谈及专业背景（发言人2为俄语专业但未从事相关职业，发言人1学数学与统计，发言人4学软件工程）。后半段发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法，但发言人5表示不懂，讨论未深入，因设备与人员安排中断。以分享为主，未形成明确结论。
+# 分段速览
+## 00:00:02-00:05:32 闲聊：阅读与综艺
+会议开场为自由闲聊。发言人1询问在场者是否看小说，发言人2表示不怎么看小说、更常刷短剧，发言人4也认同。发言人1提到自己反复阅读《红楼梦》多次，最初高中时读不太懂，反复读后才觉得有意思。话题随后转向综艺，发言人2和发言人4表示看电视剧和综艺较多，偏好娱乐类、旅游类、户外类及做饭类内容。发言人1介绍《种地吧》综艺，参与者为十个男生，走偶像路线但选择小众的种地题材，录制周期约半年、几乎24小时录制，十人后来组成组合并开演唱会。发言人1还提到英国种地综艺《克拉克森的农场》。
+## 00:05:32-00:08:15 闲聊：农业项目与专业背景
+发言人1继续介绍《种地吧》参与者成立农业公司尝试新型农业，种植小月季和水培蔬菜，有项目盈利也有项目亏损，参与者是实际股东、每人出资，但个人主要收入仍来自综艺。发言人1指出农业门槛较高，种月季需请专人照看水土。随后话题转向专业背景：发言人2是俄语专业但就业时未从事相关工作，称五六年不用已遗忘；发言人1之前学数学、后来学统计；发言人4学软件工程，属工科。
+## 00:08:15-00:12:43 闲聊：护发话题与人员安排
+发言人2称赞发言人4头发多，引发洗发水话题。发言人4表示换着用多种洗发水，目前囤有三种，称换用后头发没那么容易油了，但记不清所用品牌。发言人2询问是否有推荐，发言人4表示稍后找订单告知。随后发言人1结束录制，发言人5接手安排后续录制，涉及中英混播、八爪鱼、金融等人员与设备协调，现场出现人员调度与会议室安排，发言人2表示「不该来这个」。
+## 00:12:43-00:13:02 日本现代化转型讨论
+发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法，并指出发言人5在日本上学、应是主场。发言人5表示对日本现代化转型话题不懂。讨论因设备与人员安排中断，未深入展开。
+# 要点梳理
+## 个人阅读与综艺观看
+- **发言人1**：反复阅读《红楼梦》多次，高中初次阅读时不太能读懂，反复读后才觉得有意思。
+- **发言人2**：不怎么看小说，刷短剧更多；平时看电视剧和综艺多一点。
+- **发言人4**：不怎么看小说，看综艺多一点，娱乐类为主，烧脑类看得少。
+- **发言人1**：介绍《种地吧》综艺，参与者为十个男生，走偶像路线但选择小众路线，大部分搞音乐，后来组成组合并开演唱会。
+- **发言人1**：介绍《种地吧》录制情况，几乎24小时录制，一录半年，视频素材特别多。
+- **发言人1**：提到《种地吧》参与者成立农业公司，尝试创业发展新型农业；项目有亏有盈，参与者是实际股东，每人掏钱。
+- **发言人1**：提到《种地吧》种植小月季和水培蔬菜，月季需请专人看水和土，外行人很难做；有一个鱼塘但未认真经营。
+- **发言人1**：提到英国种地综艺《克拉克森的农场》。
+- **发言人1**：提到近期三农主题内容较多，挺多人喜欢看。
+## 专业背景与职业
+- **发言人2**：俄语专业，就业时未从事俄语相关工作，五六年没用已遗忘。
+- **发言人2**：提到康鹏曾科普俄罗斯人贸易相关信息，称其生意内部消化较多、对外营销较少，不怎么外传。
+- **发言人1**：之前学数学，后来学统计，一直是理科生。
+- **发言人4**：理科生，学软件工程，属于工科。
+## 洗发水话题
+- **发言人4**：洗发水换着用，家里囤有三种轮着用；之前头发容易油或痒，换用后没那么容易油了。
+- **发言人4**：未使用海飞丝，所用品牌不认识、叫不上名字，答应之后找订单告诉发言人2。
+## 日本现代化转型讨论
+- **发言人6**：提议讨论日本现代化转型，涉及明治维新与和平宪法。
+- **发言人5**：表示对日本现代化转型话题不懂。
+- **发言人6**：提到发言人5在日本上学，称其是主场。
+- **发言人5**：因设备与人员安排（八爪鱼、金融相关事务），讨论未深入即中断。</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5310/1910</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="13.5" customHeight="1" s="9">
       <c r="A44" s="6" t="inlineStr">
@@ -14632,6 +15427,101 @@
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t># 讲座概况
+主讲人系统梳理了朝鲜半岛从分裂到统一再到二战后分裂的历史脉络，重点讲解朝鲜战争爆发背景、主要战役、停战协定及战后影响，并现场解答听众关于朝韩现状、旅游、军队战斗力、中美关系等提问。讲座面向对朝鲜战争历史及半岛现状感兴趣的听众，围绕朝鲜半岛历史与朝鲜战争、朝鲜旅游与现状、半岛分裂原因与统一展望、韩军表现、抗美援朝决策与中美关系、中俄朝关系与图们江出海口等板块展开。核心判断包括：朝鲜战争奠定中国强国地位，美国在越南战争中未敢越过北纬十七度线；朝韩仅名义停战，三八线悲剧延续至今；韩军战斗力在1952年前弱、之后不可小视。关键锚点：1950年6月朝鲜战争爆发、1953年7月27日停战协定、1950年10月19日志愿军跨过鸭绿江。对听众而言，有助于理解朝鲜半岛问题的历史根源与当前东北亚格局。
+# 核心观点与论证
+## 朝鲜战争爆发背景与各方称谓
+- **三八线形成**：1945年二战结束、日本投降后，美苏军队分别开进朝鲜半岛南北，以北纬38度为基准形成三八线；此前半岛历经高丽、百济、新罗从分裂到统一，二战后再次分裂。
+- **苏联鼓动朝鲜南进**：1949年新中国宣布废除列强在华一切租界及特权，含苏联在东北的中长铁路及大连、旅顺特区利益；苏联不甘心，鼓动朝鲜进攻韩国，希望以仁川或釜山替代旅顺、大连地位，继续在亚洲发挥影响力。
+- **战争爆发与各方称谓**：1950年6月北朝鲜军队率先越过三八线南攻，朝鲜战争爆发；朝鲜称`祖国统一解放战争`，中国称`抗美援朝`，韩国称`625事件`，美国及西方称`朝鲜战争`或`韩战`（韩战主要为台湾地区称谓）。
+- **初期战况与仁川登陆**：战争开始后朝鲜人民军从三八线打到洛东江环形防御圈（今大邱至釜山一带）；1950年9月15日美军仁川登陆成功，将深入韩境的朝鲜人民军分割包围、逐次歼灭，收复三八线以南领土。
+## 中国出兵与主要战役进程
+- **中国出兵决策**：联合国军由美军主导、16国共同出兵，总司令麦克阿瑟欲扩大战果吞并整个北朝鲜；因朝鲜半岛对中国呈`唇亡齿寒`状态，美军越过三八线后，中国决定以志愿军形式出兵。
+- **入朝时间线**：1950年10月19日志愿军跨过鸭绿江，10月25日与韩国军队首次交火，11月5日第一次战役结束；此后相继进行第二次战役（含长津湖战役）、第三次战役。
+- **推进至三七线**：第三次战役越过三八线，占领汉城（今首尔）及仁川、水原一带，将战线推进至北纬37度；后期美军反攻，双方在三八线与三七线之间鏖战。
+- **第五次战役与停战**：第五次战役为最后一次大规模战役，结束后双方在三八线基础上互有攻防；西部中朝方面占领开城、延安半岛、望京半岛，东部美军占领襄阳、金刚山地区（金刚山今为韩国著名旅游景点）。
+- **停战协定**：1953年7月27日双方正式达成停战协定并延续至今，朝韩仅名义上停战、未实现真正和平；三八线非军事区（DMZ）与金刚山现为旅游景点。
+## 朝鲜战争的历史影响
+- **奠定中国强国地位**：从中国角度，战争奠定强国地位，美国再不敢小瞧中国；1967年越南战争时期中国警告美国不得越过北纬十七度线（南越与北越边境线），否则中国必将出兵越南，美国未敢逾越。
+- **美国称被遗忘的战争**：联合国军最后一任司令官马克·克拉克承认，他是美国历史上第一位在未取得胜利情况下签署停战协议的司令官；美国称此战为`被遗忘的战争`。
+- **朝韩两败俱伤**：伤害最深的实为朝鲜和韩国——双方本是一脉相承的血肉同胞，却分裂成两个国家，三八线悲剧延续至今。
+## 朝鲜半岛分裂原因与统一展望
+- **美苏冷战布局**：美国在三八线以南单独建立韩国，是为保护日本免遭苏联及共产主义势力影响；苏联则需在亚洲建立卫星附属国，故扶植北朝鲜独立建国，奉行对苏马首是瞻政策。
+- **统一计划落空**：最初计划像奥地利一样在不同占领区受降后举行普选、建立统一民选政府；但美苏关系急转直下，所扶植领导人各有心思，因意识形态不同最终建立两个国家，成为朝鲜战争爆发缘由。
+- **若美国未下场的假设**：若朝鲜战争爆发时美国未救援韩国，今日朝鲜可能成为苏联卫星国，既是牵制中国的钉子，也是威胁美国在亚洲（尤其日本）的定时炸弹。
+- **统一前景判断**：朝韩若统一大概率是韩国兼并朝鲜——经济影响和综合实力摆在那里；但北方有充足优质兵源及核武器、导弹等尖端武器，统一后对整个东北亚都是不稳定定时炸弹。
+- **越南类比**：越南统一第二年即进攻柬埔寨和泰国，中国被迫于1979年出兵发动对越自卫反击战；越南尚且如此，朝鲜半岛统一后局势更不可控。
+## 韩军战斗力评价
+- **初期表现差**：1950年6月25日战争爆发后，韩军因瞎指挥差点被朝鲜团灭；7月10日以后南部地面战斗主要由美军与朝鲜人民军进行，韩军初期只负责`冲人头`角色。
+- **1952年转折**：1952年后美军重新整训韩军，韩军才形成基本战斗力；此前对美军而言类似`猪队友`，志愿军与美军占不到便宜时常从韩军战线突击，美军每次兵败多由韩军战线崩溃引起。
+- **第五次战役溃败**：第五次战役中志愿军从朝鲜半岛东部对韩军形成反包围突击，打崩其前线；美国人在韩国领土上撤销了韩国第三军团。
+- **军队构成与文化**：韩军军官主体是二战时期日本扶植的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁强征的农村青年；贯彻昭和日军武士道精神，老兵欺负新兵、军队霸凌事件延续至今，被视为旧日军部队的延伸。
+## 抗美援朝而非收复台湾的决策
+- **海军实力不足**：台湾海峡距离约100公里，中共刚建国没有相应海军实力，无法进行解放台湾的战斗。
+- **美国介入台海**：1950年朝鲜战争爆发后，美国参众两院视其为共产主义世界对自由世界的全面进攻，将台湾和韩国共同纳入亚太保护圈；美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。
+- **唇亡齿寒的必然选择**：美军越过三八线向中朝边境进发，触动中国敏感神经，即便不愿与美国爆发全面战争也不得不打；既然海上无法战斗，就在陆地上战斗——长津湖和上甘岭两场战役接连让美军惨败，至今仍是美国人挥之不去的梦魇。
+## 当前美朝关系与中俄朝关系
+- **美国忌惮中俄**：美国因惧怕朝鲜背后的中国和俄罗斯而未主动进攻朝鲜——朝鲜战争时中国出动志愿军、苏联提供空军掩护和武器后勤支持，联手把美国打回三八线以南；美国不敢再次挑起半岛武装冲突。
+- **朝鲜不敢贸然动武**：金家担心江山一旦贸然发动战争会被重新颠覆，故也不敢发动战争。
+- **图们江出海口问题**：中俄朝关系`各怀鬼胎`，图们江出海口问题至今未解决——图们江是俄罗斯与朝鲜的界江、通往日本海的出海口，但俄朝建了一座小桥，大船无法通行；俄朝都不希望中国过分强大，不愿让出出海口。
+# 金句总结
+&gt; 唇亡齿寒。
+- 讲到美军越过三八线、进犯中朝边境时，说明中国决定出兵朝鲜的原因。
+&gt; 美国再也不敢小瞧我们了。
+- 总结朝鲜战争对中国国际地位的影响，并引出越南战争时期中国警告美国不得越过北纬十七度线。
+&gt; 他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。
+- 引用联合国军最后一任司令官马克·克拉克的自述，说明美国对朝鲜战争的定性。
+&gt; 伤害最深的其实还是朝鲜和韩国，毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家。
+- 评价朝鲜战争对朝韩两国的伤害，指出三八线悲剧延续至今。
+&gt; 各怀鬼胎。
+- 回答中国、俄罗斯、朝鲜三国关系现状时，指出三国各有自身利益考量。
+&gt; 既然海上没办法进行战斗，那就只能在陆地上进行战斗。
+- 解释新中国为何选择抗美援朝而非解放台湾，强调当时解放军陆军优势与海军短板。
+&gt; 长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。
+- 总结抗美援朝中两场关键战役对美军的震慑作用。
+# Q&amp;A 环节
+**听众**：这场战争开始和结束时，韩国和朝鲜的势力有很大差别吗？战争的改变大吗？
+**主讲人**：从中国角度说，奠定了我们强国地位，美国再不敢小瞧我们，导致1967年越南战争时中国警告美国绝不允许越过北纬十七度线，美国未敢越线。这场战役在美国被称为被遗忘的战争，联合国军最后一任司令官克拉克承认他是美国历史上第一次在未取得胜利的情况下签署停战协定的司令官。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
+**听众**：现在越南还分南北吗？
+**主讲人**：没有，越南是统一的，美国最终放弃了南越，北越趁机会把南越统一了。
+**听众**：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
+**主讲人**：当然是韩国更好玩。朝鲜旅游没有人身自由，入境第一件事搜手机检查，没有无线网，只有平壤有他们自己的网络运营商，类似咱们国家八九十年代的状态，手机很落后很慢，国际漫游和网络非常贵。那几天就是参观主体思想和社会主义辉煌建设成就，类似以前文革时期那种无产阶级高于一切的思想，活在异次元的世界当中。
+**听众**：他们普通人可以上网吗？
+**主讲人**：普通人不能上网，局域网都很有限，普通人连电脑和5G手机都用不起。因为外部有韩国，韩国用韩剧作为意识形态宣传武器，老百姓知道真相后会颠覆政权，否则为什么那么多朝鲜老百姓吃不饱肚子还往韩国跑？鲜有韩国人会去朝鲜，就是脱北者。
+**听众**：他们有拿飞机往朝鲜发传单，发韩国文化那种图，文化入侵？
+**主讲人**：有的，朝鲜严防，只要被发现谁家私藏，肯定要追究连带责任。
+**听众**：朝鲜那边有啥好玩的？
+**主讲人**：也就平壤那边看看志愿军抗美援朝的功绩，还有开城，毕竟是朝鲜半岛三千年古都，特产小人参。
+**听众**：朝鲜有他们古代的文化吗？高丽，还有韩剧里讲朝鲜古代将军什么的。
+**主讲人**：朝鲜半岛文明是中华文明的一个衍生物，文明有3500年历史，最早是商周时期形成初步文明。高丽半岛一直是中华文化圈的一个附属国，一直到甲午战争清朝战败后，朝鲜才彻底脱离和中国的隶属关系，成立大韩帝国，后来跟日本合并，二战后复国又被分裂。
+**听众**：朝鲜是不是和北京或俄罗斯有一个很大的广场？平壤的金日成广场，是以领导人命名吗？
+**主讲人**：对，以领导人来命名，他们大将军、大元帅这样的。
+**听众**：南北之间的割裂有什么历史渊源？为什么会成为两个政权？
+**主讲人**：一开始美国和苏联都希望在朝鲜半岛建立缓冲区。美国在分出三八线以南单独建立韩国，是为了保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建立卫星附属国，所以宣布北朝鲜独立，奉行对苏联马首是瞻的指示。两边最初诉求本来是在不同占领区受降后，像奥地利那样普选建立统一民选政府，但美苏关系恶化得非常快，所扶植的领导人也各有心思，由于意识形态不同，最终建立了两个不同国家，这也是朝鲜战争爆发的缘由。
+**听众**：当时美国没有打败朝鲜，你觉得现在美国对朝鲜的态度是怎样的？
+**主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争爆发时朝鲜快被美国完全占领，中国出动志愿军帮着朝鲜把美国打回去，苏联也提供了空军掩护和武器后勤支持，中苏联手把美国打回三八线以南。美国比较忌惮，没有主动进攻朝鲜，也没再次挑起半岛武装冲突。朝鲜金家也担心贸然发动战争后江山被颠覆，所以也不敢贸然发动战争。
+**听众**：现在的朝韩对立可以认为是韩国和西方国家在背后支撑，是一个微妙的平衡。如果当时没有形成冷战布局、互相争夺半岛控制权的话，大一统的朝鲜半岛会是什么形态？大号的朝鲜还是平衡的韩朝？
+**主讲人**：如果朝鲜战争爆发时美国没有下场救援韩国，今日朝鲜可能会是苏联卫星国附属之下、用来牵制咱们国家的一颗钉子，也是威胁美国在亚洲尤其是日本的不稳定定时炸弹。现在朝韩要是统一，大概率是韩国兼并朝鲜，毕竟经济影响和综合实力摆在那儿；但北方有充足优质兵源以及核武器和导弹尖端武器，统一后对整个东北亚地区都是一颗不稳定的定时炸弹。当年越南统一时宣布继承法国在中南半岛所有地盘，统一第二年就去进攻柬埔寨和泰国，被逼到79年出兵对越南发动自卫反击战。越南尚且如此，朝鲜半岛统一之后局势更加不可控。
+**听众**：你感觉现在中国、俄罗斯和朝鲜之间关系怎么样？
+**主讲人**：各怀鬼胎。咱们和朝鲜、俄罗斯的问题主要是图们江出海口问题，到今天还拖着没着落。
+**听众**：什么出海口？
+**主讲人**：图们江是俄罗斯和朝鲜的界江，那个地方是日本海的出海口，在中朝俄边境那块，国际水域航道可以通行，但俄罗斯和朝鲜建了一座小桥，大船没法过去。俄罗斯和朝鲜都不希望咱们过分强大，不想过多依附于我们，所以把图们江出海口封死了，都不想把出海口让给我们。
+**听众**：你觉得朝鲜战争中朝鲜军队和韩国军队有没有发挥什么作用？
+**主讲人**：一开始韩国军队瞎指挥，差点被朝鲜团灭。6月25日战争爆发，7月10日以后南部地面战斗主要是美军和朝鲜人民军打，韩军一开始负责冲人头。差不多1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力。在此之前韩军对美军来说像猪队友，志愿军跟美军占不到便宜时都从韩国军队战线突击，美军每一次兵败都是韩国军队战线崩溃引起的。第五次战役中志愿军从朝鲜半岛东部形成反包围突击，把整个韩国军队前线打崩，美国把韩国第三军团全部撤销，是美国人在韩国领土上把韩国军队给撤销了。韩军战斗力1952年之前我不敢恭维，1952年之后还是不可小视。韩军军官主体是二战时期日本人扶植起来的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁强征的农村青年。韩军从朝鲜战争成军一直到现在，贯彻二战时期昭和日军那套武士道精神管理体制，老兵欺负新兵、军队霸凌事件一直蔓延到今天，是一支充满昭和军国主义思想余孽的旧日军部队延伸。
+**听众**：1950年援朝时中国刚成立，实力不是很强，为什么选择抗美援朝而不是收复台湾？
+**主讲人**：台湾和大陆之间有一道漫长海峡，距离差不多100公里左右。中共刚刚建国，没有相应海军实力。50年朝鲜爆发战争，美国参众两院普遍认为这是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，一来防止解放军解放台湾，二来防止国民党反攻大陆。解放军建军时没有相应海军实力，没办法进行解放台湾的战斗。但美国后期越过三八线向朝鲜及中朝边境进发，触动了咱们的敏感神经，唇亡齿寒概念深入人心，导致即便不愿意和美国爆发全面战争，又不得不进行。台湾那事已经让咱们很被动，朝鲜半岛这场既然要争取战略主动，解放军陆军很强，海上没办法战斗，就只能在陆地上战斗。这也是后来战斗意志的体现，长津湖和上甘岭接连让美军惨败，这两场战役到今天也是美国人挥之不去的梦魇。</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7464/6160</t>
         </is>
       </c>
     </row>
@@ -14815,6 +15705,54 @@
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>对话记录</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t># 对话概况
+本次闲聊由发言人1以“出门必带的三样东西是什么”提问开场，五名发言人围绕个人随身物品习惯展开漫谈，话题从必带物品（手机、充电宝、指甲刀、钥匙、皮圈、耳机、工卡等）自然延伸至头发打理与个人形象，再因提及“秋天容易下雨”转入北京降雨与居住安全讨论。主要话题包括：出门必带物品、钥匙与电子锁使用习惯、头发打理与形象偏好、留长发胡子的个人经历、北京降雨季节性与低洼居住风险。倾向与差异方面：多数人认可手机必带，分歧主要在“必要”与“安心”之间——发言人2以指甲刀平替钥匙、上班必带刮胡刀（平均每三天一次，因胡子一天能长几毫米），发言人5则每日带手机、耳机和工卡；关于绑发与披发，发言人1认为散头发更好看，发言人2表示若自己是女生会选择披发，因绑发显得脑袋大。整体以分享为主，未形成明确结论。可作锚点的事例包括：发言人2胡子一天长几毫米、平均每三天带一次刮胡刀上班、发言人2留胡子时曾被误认为新疆少数民族。
+# 交流内容
+- **出门必带物品**：发言人1起头问出门必带三样东西，发言人2答`手机`、`充电宝`、`指甲刀`，称指甲刀可磨手掌、戳钥匙；发言人3答`钥匙`，发言人1附和必须带钥匙；发言人4表示必带绑头发的`皮圈`；发言人5称每天带`手机`、`耳机`和`工卡`。
+  - 发言人2已用`电子锁`多年、没有钥匙概念，用指甲刀平替钥匙；还提到以前`扣耳勺`也挂钥匙上。
+  - 发言人4担心钥匙破坏性强，倾向套起来或挂起来；发言人1称自家门是`指纹锁`，出门只需`手机`和`充电线`。
+  - 发言人2上班必带`充电宝`、`手机`、`刮胡刀`三件套，平均`每三天`带一次刮胡刀，因胡子`一天能长几毫米`；发言人5的耳机和工卡直接放单位，靠`刷脸`进门。
+  - 发言人1提到领`夜宵`需带工卡，发言人2称领完即把工卡扔回工位；发言人3补充出门带`纸巾`、下雨带`伞`。
+- **头发打理与个人形象**：发言人2好奇初中男生爱薅女生`头发圈`的原因，发言人1表示无此爱好、认为散头发比绑发好看；发言人2称若自己是女生会披发，因绑发显得`脑袋大`；发言人3建议弄个`公分`两边补点小点。
+  - 发言人2曾想留长发配大胡子，因不好打理放弃；尝试留胡子时被误认为`新疆少数民族`。
+- **下雨天气与居住安全**：发言人1称秋天容易下雨，发言人2好奇为何不是春天；发言人4认为`北京`夏天易下雨，发言人1补充北京下雨少、无季节性。
+  - 发言人3提到每年下雨`园区门口`都是水，`李博`家曾被淹；发言人2建议住`三楼以上`，远离低洼风险。
+# 关键原话
+&gt; 手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。
+- 发言人2回答发言人1提出的“出门必带三样东西”问题，解释指甲刀的多重用途。
+&gt; 对呀，我必须带钥匙，不带钥匙就行。
+- 发言人1回应发言人3提到的“钥匙”，强调自己出门必带钥匙。
+&gt; 我我已经好多年的电子锁了，我都没什么钥匙的概念了都。然后所以说拿指甲刀来平替钥匙了。
+- 发言人2说明自己因长期使用电子锁而用指甲刀替代钥匙。
+&gt; 我一定会带一个那个皮圈就绑头发的。
+- 发言人4在讨论出门必带物品时提到必带绑头发的皮圈。
+&gt; 对，所以说我上班必带三件套，充电宝、手机、刮胡刀。
+- 发言人2总结自己上班必带物品，此前提到胡子一天能长几毫米、平均每三天带一次刮胡刀。
+&gt; 我现在每天就是手机、耳机和工卡。
+- 发言人5回应“没人上班带耳机吗”，说明自己每天必带物品。
+&gt; 我觉得北京是夏天能易下雨的。
+- 发言人4回应发言人2关于“秋天容易下雨”的疑问，提出北京夏天易下雨。
+&gt; 是我记得每年的下雨，嗯，都都那个园区门口都是水。李博还之前不是还就是开幕的那个地方还被淹了吗？
+- 发言人3在讨论下雨天气时提到园区门口积水及李博家曾被淹。
+# 共识与分歧
+- **共识**：**出门必带物品以实用与个人习惯为核心**，多数人认同手机、钥匙、充电宝等属于高频刚需，理由集中在“不带会带来实际不便”（如发言人1强调“不带钥匙不行”、发言人2因胡子长得快而必带刮胡刀），分歧主要落在“必要”与“安心”之间——如发言人2用指甲刀平替钥匙、将充电宝视为“既能充电也能防身”的物件，属于习惯性安心；而发言人5带耳机、工卡则更贴近工作场景的必要性。
+- **分歧**：在头发打理上呈现审美差异——发言人1认为散头发比绑发好看，发言人2从自身角度认为绑发显脑袋大、倾向披发，发言人4则因实际需要（绑头发）必带皮圈；在天气判断上存在经验差异——发言人4认为北京夏天易下雨，发言人1认为北京下雨少且无季节性，发言人3以园区门口积水、李博家被淹为例佐证夏季暴雨风险，发言人2据此提出“住三楼以上”的居住安全建议。
+- **倾向**：本场为分享漫谈型，未形成明确结论，整体倾向是**出门物品因人而异，以个人习惯和实际场景为转移**；对居住安全的讨论虽由天气引出，但发言人均以自身经验或听闻为依据，未上升到统一行动建议。
+# 延伸话题与后续
+- **秋天容易下雨还是春天容易下雨**：发言人1提到秋天容易下雨，发言人2好奇为何不是春天，发言人4认为北京夏天容易下雨，发言人1补充北京下雨少且无季节性，讨论未形成定论。
+- **李博家被淹的后续**：发言人3提到每年下雨园区门口积水，李博家曾被淹，发言人2建议住三楼以上，未再深入。</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3851/2252</t>
         </is>
       </c>
     </row>
@@ -15008,6 +15946,51 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为开放式漫谈，由发言人1发起，围绕“手机里最常用的三个APP”展开，共5位成员（发言人1至发言人5）参与，无正式议程。讨论由常用APP话题自然延伸至AI助手、视频播放器、音乐平台及歌手偏好等议题，具体包括：常用APP与AI助手使用习惯、视频与播放器APP使用情况、音乐APP与音乐偏好。整体以分享个人使用经验与观点为主，未形成统一结论。讨论按话题逐块推进，从APP清单切入，经AI助手准确性争议、视频平台版权与广告问题，过渡至音乐平台选择与听歌场景，最后以对Taylor Swift等歌手的偏好交流收尾。会议提及“单框架手机”“卓翼通”“虾扎”等专名，以及“柏林地铁”等场景锚点。
+# 发言要点
+## 常用APP与AI助手使用习惯
+- **发言人2**：最常用APP为知乎、小红书、谷歌；不常用AI软件，因不确定其回答是否正确，仍停留在浏览器、纸质地图、尺子、圆规和铅笔标注的思维模式。
+- **发言人3**：最常用微信、抖音、淘宝、京东等；已下载豆包AI助手，认为AI小助手回答更精准、总结性更强。
+- **发言人4**：最常用微信、小红书；手机用小布小布AI助手，已不用浏览器直接搜索。
+- **发言人5**：已下载豆包AI助手。
+- **发言人1**：使用百度千问等AI助手；对AI回答准确性提出质疑「你能判断他说的是对的吗」。
+## 视频与播放器APP使用情况
+- **发言人5**：常用B站和YouTube，希望中英混杂内容能被识别；指出单框架手机现在连YouTube都下不了。
+- **发言人4**：指出YouTube手机一般翻不了墙。
+- **发言人1**：发现国内付费电视剧在YouTube上免费。
+- **发言人2**：YouTube上部分内容仍需付费，但一些小网站可免费观看，因大平台有版权纠纷需付费；广告时间太长，倾向直接用B站观看。
+- **发言人3**：常用腾讯视频、爱奇艺、优酷、芒果TV等播放器；提到可通过看广告获得VIP时长。
+- **发言人5**：APP太多，不知道开哪个VIP。
+## 音乐APP与音乐偏好
+- **发言人5**：常用网易云音乐；单框架手机网易云不适配，现用卓翼通。
+- **发言人2**：以前常用酷狗、酷我；提到欧美音乐平台虾扎有更多欧美演唱会版本，但大牌音乐因版权纠纷播不出来；在柏林坐地铁时听音乐代入感强，因地铁较安静。
+- **发言人1**：认为虾扎平台唱的多是小众歌手；上班时听音乐。
+- **发言人4**：通勤路上听音乐，需用降噪耳机。
+- **发言人3**：最近喜欢谢霆锋，因其演唱会感染力强、氛围好；提到可通过看广告获得VIP时长。
+- **发言人2**：疑惑Taylor Swift为何重新火起来——2010年代开头已火，后因绯闻消沉，但对九零后和零零后影响都很深；提到其与猫头鹰之城主唱亚当杨的绯闻，称当时东南卫视台湾节目讲过。
+# 共识形成
+- **一致意见**：与会者普遍认可AI助手比浏览器更全面、回答更精准、总结性更强（发言人3），但发言人2明确表示不常用AI软件，因不确定其回答是否正确，仍停留在浏览器、纸质地图、尺子、圆规和铅笔标注的思维模式，形成**AI助手便捷性与准确性信任度**的倾向性分歧。
+- **视频平台分歧**：发言人1发现国内付费电视剧在YouTube上免费，发言人2指出YouTube上部分内容仍需付费，但一些小网站可免费观看，因大平台有版权纠纷；发言人2抱怨播放器广告时间太长，倾向直接用B站观看，发言人3提出可通过看广告获得VIP时长。
+- **音乐平台分歧**：发言人2提到欧美音乐平台虾扎有更多欧美演唱会版本，发言人1认为其多为小众歌手，发言人2指出因版权纠纷大牌音乐播不出来；发言人5因单框架手机网易云不适配，现用卓翼通。
+- **歌手偏好**：发言人3最近喜欢谢霆锋，发言人2疑惑Taylor Swift为何重新火起来，称其2010年代已火，后因绯闻消沉，未得到明确解答。
+# 待探讨问题与后续
+- **未定论**：发言人2疑惑Taylor Swift为何在近期重新火起来，称其2010年代已火、后因绯闻消沉，但未得到明确解答。
+- **未确认**：发言人2提及Taylor Swift与猫头鹰之城主唱亚当·杨曾传出绯闻，并称其当时曾向对方表白，发言人4表示未关注此事，该说法未获其他成员证实。
+- **未确认**：发言人2提到欧美音乐平台「虾扎」有更多欧美演唱会版本，但发言人1认为其多为小众歌手，发言人2指出因版权纠纷大牌音乐播不出来，该平台的具体情况未进一步核实。
+- **待核实**：发言人5指出单框架手机网易云音乐不适配、需用「卓翼通」替代，其他成员未回应，该问题是否普遍存在未获讨论。</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4259/1974</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="13.5" customHeight="1" s="9">
       <c r="A47" s="6" t="inlineStr">
@@ -15179,6 +16162,64 @@
           <t>专题讲座</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次讨论由主持人（发言人1）发起，围绕2022年俄乌战争以来俄军的战场表现展开，对比游戏与影视中的俄军形象，并延伸至俄罗斯的地缘政治认知、旅游与文化印象。讨论面向对军事、地缘政治及俄罗斯文化感兴趣的参与者，以开放座谈形式进行。板块涵盖俄军在俄乌战争中的实际表现、游戏与影视中的俄军形象、俄罗斯的地缘政治与欧洲认知、俄罗斯旅游与文化印象。核心判断包括：俄军单兵素质强但后勤与指挥拉垮，形容为“矮脚巨人”；俄军从闪电战转为持久战，双方重装备耗尽，陷入战壕对峙与无人机互炸状态；欧洲将乌克兰视为“欧洲之门”，将俄罗斯视为亚洲游牧民族，因此支持乌克兰以阻挡俄罗斯。锚点案例包括《战地风云》《使命召唤》《红警》等游戏中的俄军形象、圣彼得堡东宫（世界四大艺术博物馆之一）、俄罗斯以探险队名义掠夺多国藏品。对听众而言，有助于理解俄军表现背后的多重因素及俄罗斯与欧洲的地缘认知差异。
+# 核心观点与论证
+## 俄军表现与预期严重不符
+- **战争预期落空**：2022年俄乌战争爆发时，全世界认为战争天平会向俄罗斯一边倒，基辅会很快被占领、乌克兰会被消灭、泽连斯基会流亡；实际泽连斯基扛住进攻，俄军被从基辅打回白俄罗斯和乌克兰边境。
+- **从闪电战变持久战**：俄军基层官兵收到命令时以为是去演习，结果演着演着进入乌克兰；第一批部队遭遇的是民兵自发抵抗而非军队有组织进攻，一来二去从闪电战变成持久战。
+- **战场形态退化**：双方重装备耗光后，只能隔着战壕互相扔手雷或用无人机互炸，发言人1形容为「从钢铁洪流变成了菜鸡互啄」；发言人4认为俄乌战场与二战相比没多大进步，只是多了无人机。
+- **单兵强而体系弱**：发言人1总结俄军「单兵素质很厉害，但总体很拉垮，主要后勤和指挥上」，形容为「矮脚巨人」——像柯基一样腿短撑不起庞大身躯。
+## 俄军表现不佳的原因分析
+- **普京信息茧房**：发言人1认为普京「活在他自己的信息茧房里」，对战场真实情况缺乏准确判断。
+- **情报经费被贪污**：用于策反乌克兰官员的经费被情报官员贪污瓜分，普京真要进攻时乌克兰高官根本没收到策反经费。
+- **乌克兰民族仇恨**：2014年俄罗斯占领克里米亚后，乌克兰上下迸发民族仇恨，发言人1类比为「九一八事变」式耻辱——一枪不发丢掉整个克里米亚，民众对政府无能与腐败非常不满。
+- **装备依赖伊朗**：发言人1指出俄罗斯的无人机靠伊朗提供，乌克兰则靠北约持续输血，形成类似越战的消耗战格局。
+## 游戏与影视中的俄军形象
+- **游戏形象与现实反差**：发言人1提及《战地风云》《使命召唤》《红警》等游戏中的俄军或苏联红军形象，与现实中俄军表现有「360度的改观」。
+- **西方游戏刻意抹黑**：发言人2认为《红警》是美国为黑苏联而制作；发言人4补充称西方主导的游戏几乎都把苏联描绘成反面角色——很猛、很变态、研究邪乎武器、规模夸张。
+- **意识形态丑化**：发言人1指出西方把共产主义解放世界的思想抹黑成`心灵控制器`（《红警》中的武器），把毛子形容成暴力美学的形象代言。
+## 欧洲地缘认知与乌克兰地位
+- **欧洲之门**：乌克兰在欧洲人认知中被称为`欧洲之门`；欧洲人认为欧亚分界线在乌克兰而非乌拉尔山脉——白俄罗斯大部分是沼泽地，无法形成大规模运输通道走廊。
+- **俄罗斯被当亚洲人**：欧洲人把俄罗斯人当亚洲野蛮人看待，类似《冰封王座》中贝加尔湖一带半兽人的反派角色；俄罗斯被蒙古人统治二百年，不被欧洲认可接纳，被视为「长着欧洲面孔的亚洲游牧民族」。
+- **欧洲支援乌克兰的动机**：欧洲必须武装并守好乌克兰，把俄罗斯挡在亚洲之外；若俄罗斯握紧乌克兰，欧洲会「再一次生活在曾经的阴影之下」——唇亡齿寒的道理欧洲人明白。
+- **美国与欧洲态度差异**：发言人1称在美国人认知中俄罗斯「既不是朋友也不是敌人，就是一个普通国家」；但在波兰、乌克兰、波罗的海三国等东欧国家眼中，俄罗斯就是敌人、蛮子、半兽人。
+## 俄罗斯旅游与文化印象
+- **东宫值得一去**：发言人1推荐圣彼得堡东宫，称其为`世界四大艺术博物馆之一`，连续三次参观不同区域都没看完馆藏珍宝，圣彼得堡夏天不错。
+- **藏品来源多元**：俄罗斯以探险队名义从全球掠夺藏品——西至德国、法国、荷兰（含二战打进德国运回纳粹产品及王室联姻赠品），东至朝鲜半岛、蒙古、西藏、西夏王陵、敦煌，南至阿富汗、中亚、埃及、北非、奥斯曼帝国土耳其。
+- **签证与入境经历**：发言人2提到去俄罗斯旅游后办美签可能被拒；发言人1分享因多次去俄罗斯，在美国边境入口被拦下盘问去俄目的，差点被怀疑是间谍。
+# 金句总结
+&gt; 俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上。
+- 讲到俄军在俄乌战争中的整体表现，针对其单兵能力与后勤指挥体系的落差。
+&gt; 从一种钢铁洪流变成了最后的菜鸡互啄。
+- 讲到双方重装备耗尽后，战场陷入战壕对峙与无人机互炸的状态。
+&gt; 没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。
+- 讲到俄罗斯必须将乌克兰握在手中的地缘政治原因。
+&gt; 欧洲的边界是在乌克兰，一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。
+- 讲到欧洲支援乌克兰以阻挡俄罗斯、避免欧洲再次生活在阴影下的战略考量。
+&gt; 长着欧洲面孔的亚洲游牧民族。
+- 讲到欧洲人因俄罗斯被蒙古统治二百年而不予认可，将其视为亚洲人的认知。
+# Q&amp;A 环节
+**发言人4**：俄罗斯打仗是不是得给它打到要家破国亡了，才能迸发出战斗力打防守反击？主动进攻感觉就不行。
+**发言人1**：可以这么说。俄军单兵素质很厉害，但总体拉垮，主要在后勤和指挥上，像“矮脚巨人”，腿特别短，支撑不起庞大的身子。2022年开战时普京活在自己的信息茧房里，底下情报官员把策反乌克兰官员的经费全贪污瓜分了，没想到普京真会进攻；基层官兵也以为是去演习，结果演着演着就进了乌克兰，第一批部队遭遇的是民兵自发抵抗，不是军队有组织进攻，一来二去从闪电战变成了持久战。
+**发言人4**：感觉俄乌战场打得跟二战时候也没啥进步，多了点无人机，还是扔手雷，不太先进。
+**发言人1**：双方重装备都耗光了，只能隔着战壕互相扔手雷、用无人机互炸，从钢铁洪流变成了菜鸡互啄。俄罗斯的无人机靠伊朗给，乌克兰靠北约持续输血，有点像越战的形式——乌克兰相当于北约，俄罗斯相当于越战时的美国，就这么耗着。
+**发言人2**：去俄罗斯旅游之后，签证上会留记录，办美签的时候会被拒吧？
+**发言人1**：对，我上次去美国，因为去过好几次俄罗斯，在边境入口就被拦下来盘问去俄罗斯干嘛，差点被怀疑是间谍。美国人对咱们既不当朋友也不当敌人，但东欧国家——波兰、乌克兰、波罗的海三国——是把俄罗斯当敌人、当蛮子看的。不过圣彼得堡的东宫还是值得去，世界四大艺术博物馆之一，我连续去了三次，不同区域都没逛完。
+**发言人4**：俄罗斯地域那么宽阔，远东地区和欧洲那头差别大不大？
+**发言人1**：总的来说还是以俄罗斯族为主，他们俄国东扩也像美国西进似的，源源不断淘金移民。俄罗斯历史上以探险队名义从欧洲、中东、东亚掠夺了不少藏品，东宫里能看到德国、法国、荷兰的，也有朝鲜半岛、蒙古、西藏、西夏王陵、敦煌的，还有阿富汗、中亚、埃及、北非、奥斯曼土耳其时期的藏品。</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6103/3045</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="13.5" customHeight="1" s="9">
       <c r="A48" s="6" t="inlineStr">
@@ -15276,6 +16317,56 @@
           <t>专题讲座</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次讨论由主持人发言人1组织，围绕电影《南京照相馆》展开，与会者分享了观影印象，并延伸至南京大屠杀的历史背景、真实与虚构细节及各地抗战纪念馆的参观体验。发言人1指出，电影主要人物为虚构，但照片拍摄真实，实际由两名美国传教士拍摄日军暴行，中国照片冲洗员偷偷拷贝后于战后交给国民政府军事法庭作为审判证据；中华门城墙战斗、挹江门撤退惨案及战后审判谷寿夫等主犯均为真实历史。发言人1还分析了南京大屠杀的成因，提及日军自九一八事变以来首次遭遇淞沪会战的迎头痛击、日本屠城传统及高压武士道精神，并指出松井石根曾下令避免烧杀抢掠，因生病被替换后，朝香宫鸠彦亲王发布“不留俘虏”命令导致军纪失控。与会者还分享了沈阳伪满洲国博物馆、唐山大地震纪念馆、上海淞沪会战纪念馆等地的参观经历，并提及南京大屠杀纪念馆预约困难。本次讨论面向对历史题材电影及抗战历史感兴趣的听众，有助于厘清电影叙事与史实的边界，深化对南京大屠杀历史成因与记忆传承的认识。
+# 核心观点与论证
+## 电影主要人物虚构，照片拍摄真实
+- **人物虚构**：电影中主角与日本军官建立友谊的情节为虚构，发言人1确认主要人物并非真实历史人物。
+- **照片真实**：照片拍摄本身真实，但方式与电影描述不同——实际由两名美国传教士拍摄日军暴行。
+- **照片来源**：当时一名负责为日本人冲洗照片的中国冲洗员无意间发现日军暴行照片，因属日本禁文而偷偷拷贝藏起。
+- **照片用途**：抗战结束后，该冲洗员将照片递交给国民政府军事法庭，作为审判日本战犯的证据。
+## 南京大屠杀历史背景与成因
+- **战争进程**：1937年8月13日国民党军队在上海与日军激战，后因实力原因撤退，日军从上海一路追击至南京。
+- **抵抗空白**：自1931年九一八事变至八一三淞沪抗战前，日军占领东北、华北均未遭遇成规模抵抗，淞沪抗战是日军首次迎头痛击。
+- **军纪失控**：日军因战场伤亡惨重、长达四个月作战已杀红眼，攻破南京后缺乏法律与军纪约束，导致南京大屠杀发生。
+- **日军心态**：发言人1分析日军遭受前所未有的侮辱感与战场应激创伤，结合日本攻破城镇后屠城的传统，以及高压武士道精神下的欺凌与霸凌背景，日军以放纵作为宣泄。
+## 松井石根与朝香宫鸠彦的指挥更替
+- **松井石根命令**：原日军指挥官松井石根因生病被临时替换，他曾接连发布命令，要求避免日军在上海至南京沿线烧杀抢掠，以免招致中国军民反感、增强抵抗意志。
+- **朝香宫鸠彦接任**：接任者为裕仁亲王的叔叔朝香宫鸠彦亲王，他是日本国内脱亚入欧思想的狂热追随者，认为亚洲国家除日本外皆低贱。
+- **不留俘虏命令**：朝香宫鸠彦上任后发布第一道命令为「不留俘虏」，日军第一时间格杀勿论，随后蔓延至对老百姓群体，最终导致南京大屠杀与日军军纪失控。
+## 电影中的真实历史细节
+- **中华门战斗**：电影开头中华门城墙的战斗是真实历史细节，反映日军进攻南京所遭受的抵抗。
+- **挹江门惨案**：电影中挹江门撤退场景真实——宪兵未让军民撤出，守挹江门部队未收到撤退命令，双方信息差导致惨案发生。
+- **战后审判**：电影尾声审判为真实历史——打进南京的谷寿夫（第六师团师团长）及多名南京大屠杀主犯（基层日军军官）当时被枪决。
+- **日本否认现状**：发言人5指出现在很多日本人不承认南京大屠杀这一事实。
+# 金句总结
+&gt; 在战场上长达四个月的一个状态，然后已经杀红眼了，就是可以说是在战争底下那种就是人性的泯灭吧。
+- 讲到日军从上海追击至南京途中军纪失控、攻破南京后发生大屠杀的成因。
+&gt; 从他们当时那样的一个心态来说，就。觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。
+- 分析日军在淞沪会战遭受迎头痛击后，其心态与后续暴行之间的关联。
+&gt; 因为从他自己的角度来说，就是说我兴许我活不到战争结束，那我就趁着我还活着的时候，我对自己进行一种放纵。
+- 解释日军攻破城镇后以屠城进行狂欢与麻痹的心理动因。
+&gt; 从上到下那种高压武士道的精神那种，哦，就是。欺凌与霸凌的这种背景之下，更想找一种宣泄口这种方式来发泄。
+- 剖析高压武士道精神背景下日军寻找宣泄口、最终导致军纪失控。
+&gt; 果然他上任之后发布的第一道命令就是不留俘虏，月后祭坟。
+- 提及朝香宫鸠彦亲王接替松井石根后发布的第一道命令，直接导致南京大屠杀。
+# Q&amp;A 环节
+**发言人4**：电影里主角和一名日本军官好像建立了友谊，这个情节是虚构的，还是真有这样的日本军官？
+**发言人1**：电影里的主要人物是虚构的，但照片拍摄是真实的，只是方式与电影描述不同。真实历史是两名美国传教士拍摄了日军暴行；同时期我国一名负责给日本人冲洗照片的人员无意间发现这些照片，偷偷拷贝藏起，抗战后交给国民政府军事法庭，作为审判日本战犯的证据。
+**发言人5**：现在好多日本人还不承认南京大屠杀这件事。
+**发言人1**：对。电影里真实的历史细节包括：开头中华门城墙的战斗是真实的；挹江门撤退时，宪兵没让平民撤出，守军未收到撤退命令，双方信息差导致惨案；电影尾声审判中，谷寿夫等打进南京的部队主犯被枪决，也是真实历史。</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4228/2161</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="13.5" customHeight="1" s="9">
       <c r="A49" s="6" t="inlineStr">
@@ -15357,6 +16448,44 @@
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论由主持人发言人1发起，参与者发言人2参与，共两人围绕日本国家概况进行交流。讨论由主持人提出“谈谈日本这个国家的概况、大家对日本的印象和了解”直接引出，无特定前情。议题范围涵盖日本历史与文化、天皇制度、社会结构、旅游与购物体验等。讨论以分享观点为主，未形成统一结论。讨论中提及日本文化经历三次转折（大化改新、明治维新、二战后和平宪法转型），以及广场协议后泡沫经济崩溃催生中古店产业等关键信息。整体推进方式为漫谈发散，由主持人主导讲解，参与者穿插提问与分享，话题从历史文化自然过渡至旅游购物。
+# 发言要点
+## 日本历史与文化
+- **发言人2**：读研时上过日本文化课程，读过老舍《四世同堂》后，认为民族仇恨还是应该要有一点影响。
+- **发言人1**：日本文化缺乏原创，多为外来接收后的本土化改进，经历三次转折——大化改新、明治维新、二战后和平宪法转型。
+- **发言人1**：大化改新后日本向中国和朝鲜半岛学习，在吴越文化基础上本土化转型，形成和服、制茶、漆器等传统印象。
+- **发言人1**：明治维新后日本向欧美列强学习，借鉴英国和德国的法度；二战后美国制定和平宪法，推动社会结构转型，形成动漫、二次元、汽车工业、铁道工业等现代印象。
+- **发言人2**：日本民族性格极端，因其为岛国、气候不稳定，如发展农业可能遭遇海啸等灾害，导致性格容易极端。
+- **发言人1**：古代天皇对各地封建君主而言更像吉祥物般存在，类似东汉末年、战国时期的天子，被供奉为神灵以精神层面控制百姓。
+- **发言人1**：1945年二战结束后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，从精神上打破固有认知以推动社会转型。
+- **发言人1**：日本现为君主立宪制，天皇及皇室成员不能参与政治和国家事务，政治由国会和内阁选出首相执政，体制与英国、西班牙相近；天皇存在感不如英国国王，因英国国王还是英联邦国家名义元首，日本只有本州岛范围。
+## 日本旅游与购物
+- **发言人1**：东京购物和博物馆资源丰富，推荐美妆、护肤品、玩具，如数码宝贝玩偶、铁甲小宝原装及数码宝贝第二部黑暗战路暴龙兽合金版均为秋叶原最早发行。
+- **发言人1**：日本奢侈品便宜，中古店（二手奢侈品商店）很多；中古店源于广场协议后泡沫经济一夜崩溃，失业上班族寄卖高档大衣、西装、皮具等催生新产业。
+- **发言人1**：中古店在上海很多，可买到LV、Burberry、古奇等上个世纪知名大牌，女性款式较多，男性款式相对有限。
+- **发言人1**：个人偏好镰仓气候，夏天去比较舒服，喜欢登山、爬富士山、逛古城和博物馆，如镰仓、京都、名古屋等关西地区有本土化改良的文化场景。
+# 共识形成
+- **一致意见**：双方均认可日本文化对当代影响深远，且其文化缺乏原创性，多为外来接收后的本土化改进；对日本旅游与购物体验评价较高，认为其在服务业与购物体验方面首屈一指。
+- **倾向性认识**：发言人1系统梳理日本文化三次转折——大化改新、明治维新、二战后和平宪法转型，并指出天皇制度从古代「吉祥物」式存在，经麦克阿瑟1945年要求天皇公开露面后，转变为无实权的象征性君主立宪制，与英国、西班牙体制相近；发言人2认同此框架，并补充认为日本民族性格极端与岛国气候不稳定有关。
+- **主要分歧点**：发言人2提出「民族仇恨还是应该要有一点影响」，发言人1回应称中日民族仇恨「没那么严重」，并对比欧洲、中亚民族仇恨更为严峻——双方对历史仇恨在当代认知中的权重存在不同侧重，未就此达成统一结论。
+# 待探讨问题与后续
+- **未确认**：日本民众现在对天皇是否仍有崇拜，发言人2提出该疑问，发言人1回应称已无崇拜、天皇为象征性存在，但未提供调查数据或民意依据。
+- **未确认**：二次元一词的英文表达，发言人1现场提问，未获明确回答，讨论随即转向其他话题。
+- **未定论**：日本民族性格与岛国气候不稳定之间的因果关系，发言人2提出该观点，发言人1未作回应或补充，该话题未深入展开。
+- **未定论**：日本文化缺乏原创性、多为外来接收后本土化改进的判断，发言人1提出此观点，发言人2未明确赞同或反对，讨论未就此形成一致认识。</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>4892/1784</t>
         </is>
       </c>
     </row>
@@ -15566,6 +16695,63 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为自由文学讨论，由发言人1提议从《西游记》延伸至《三国演义》，共5位发言人参与。讨论以三国历史细节、人物评价与阵营偏好为起点，随后转向《红楼梦》的版本、判词与人物命运。三国部分围绕诸葛亮去世后的正史后续（姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴）、赤壁印象、蜀汉阵营偏好、刘备称汉中王引发的连锁反应（吕蒙白衣渡江、夷陵惨败）、借荆州与湘水划界、单刀赴会、东吴大都督结局、魏延烧栈道及三顾茅庐与隆中对等议题展开；红楼梦部分则聚焦前八十回与后四十回作者差异、第五回判词预示结局、晴雯与袭人的人物对应、林黛玉与薛宝钗的明清解读及秦可卿前朝公主之说。讨论以分享观点为主，未形成统一结论，整体按三国、红楼梦两大议题逐块推进，发言人多以补充史实与解读的方式参与，穿插个别成员的提问与回应。
+# 发言要点
+## 三国印象与历史细节讨论
+- **发言人2**：三国到诸葛亮去世就基本差不多了，后面没意思，自己没看完；印象最深刻的章节是赤壁，认为三国前面比后面有意思。
+- **发言人2**：受《三国演义》影响，偏好蜀汉刘备阵营，理由是刘备白手起家。
+- **发言人1**：正史后续还有姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴等事件；孙权晚年昏庸，在二宫之争中害死两个儿子，导致东吴朝廷大乱。
+- **发言人1**：刘备称汉中王不妥，引发连锁反应——吕蒙白衣渡江、刘备伐吴失败（夷陵惨败）；若未称王，孙权可能不会彻底决裂。
+- **发言人1**：讲述借荆州与湘水划界细节——孙权只要求刘备归还部分地区，刘备不乐意，孙权派兵强夺荆南三郡；因曹操攻下汉中威胁西川，刘备回师并与孙权签订湘水之盟。
+- **发言人1**：单刀赴会实为鲁肃与关羽各带随从在中立区谈判，被罗贯中美化为关云长只身赴险。
+- **发言人2**：白衣渡江伪装成商人，在古代打仗不太道德、突破底线，开了坏头，吕蒙口碑不好。
+- **发言人1**：吕蒙白衣渡江偷盟友家，后世把「小偷鼠辈」与吕蒙名字画等号。
+- **发言人1**：东吴大都督结局——周瑜被曹人射毒箭阵亡，鲁肃得瘟疫病故，吕蒙病故，陆逊在二宫之争时被孙权活活逼死。
+- **发言人1**：陆逊因责备孙权立太子后不应让两子争斗，被孙权逼迫而死。
+- **发言人2**：蜀汉也内斗；对陆逊的印象主要来自三国杀，东吴后期政治斗争严重，大都督们没太闹好。
+- **发言人1**：刘禅自知能力不行，完全放权给诸葛亮；诸葛亮去世后姜维无力回天，刘禅轻信黄皓谗言；姜维是魏国降将，若非诸葛亮提拔没有说服力，众人不服他。
+- **发言人1**：魏延正史没有谋反，只是不甘心大军撤退，烧毁悬崖栈道；若非姜维断后挡住司马懿军队，后果不堪设想——无反心但行为与谋反无异，实为与杨仪的个人矛盾上升至国家层面。
+- **发言人5**：三顾茅庐——刘备中原屡战屡败，深感缺乏谋士，经人推荐得知隆中诸葛亮有卧龙之才，携关羽、张飞三次拜访，前两次未见到，第三次诸葛亮被其打动，提出隆中对战略（联合孙权），最终同意辅佐刘备。
+- **发言人1**：隆中对战略为横跨荆益、外结好孙权、西和诸戎，趁魏国变动时北伐；白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，与结好孙权相矛盾。
+- **发言人1**：诸葛亮北伐目标在关中平原和陇西（今陕西、甘肃南部），希望纵跨凉益以图中原；第一次北伐赢面大，因马谡兵败街亭而破产，后期只能拖延魏国灭蜀时间，北伐更像绝望中的抗争。
+## 红楼梦版本与人物讨论
+- **发言人4**：红楼梦可当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在是没有解开的谜底。
+- **发言人3**：红楼梦只写了前八十回，后面是别人续写的。
+- **发言人2**：有反清复明的版本解读，真正的意义估计与当时朝代、社会有关。
+- **发言人4**：第一遍读高鹗续写版本时觉得挺合理，年纪小不知道后四十回不是同一作者；反复读前八十回后再接触续写，发现林黛玉性格变了很多。
+- **发言人3**：第五回贾宝玉梦游太虚幻境，判词已把结局交代了。
+- **发言人4**：判词没有点得那么明确，探春、史湘云的结局都是猜的，最后谁和贾宝玉在一起也没说清。
+- **发言人4**：晴雯是林黛玉的替身，性格像林黛玉；袭人性格像薛宝钗；晴雯之死是曹雪芹原作所写，映照后面情节。
+- **发言人2**：有解读说林黛玉代表明朝、薛宝钗代表清朝。
+- **发言人4**：有人解读秦可卿是前朝公主；秦可卿是金陵十二钗正钗之一，可惜老早去世。
+- **发言人4**：第五回贾宝玉在秦可卿床上睡觉做梦到太虚幻境，看到判词——十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每个人命运。
+- **发言人2**：疑问为何选高鹗后四十回作为官方结尾。
+- **发言人4**：高鹗续写总体比较合理，官方说法是在残稿上梳理完善，未违背作者原意，但诗词能力不及曹雪芹。
+- **发言人3**：北京植物园旁边村子有曹雪芹小道，之前爬山看到过。
+- **发言人4**：北京植物园里有曹雪芹的故居。
+# 共识形成
+- **一致意见**：与会者普遍认为《三国演义》前半部比后半部更有意思，发言人2明确表示「三国到诸葛亮去世也基本就差不多了」，此观点未遭反驳；对吕蒙白衣渡江一事，发言人1与发言人2均认为其「开了个坏头」「突破底线」，吕蒙因此在后世口碑不佳。
+- **倾向性认识**：发言人2受演义影响偏好蜀汉刘备阵营，认为刘备「白手起家」；发言人1则指出刘备称汉中王引发连锁反应，导致吕蒙白衣渡江、夷陵惨败，双方对刘备评价侧重不同但未正面交锋。关于魏延，发言人1主张其「没有反心，但他的行为跟谋反没什么实质上的区别」，因烧毁栈道危及大军撤退。
+- **主要分歧点**：发言人2认为白衣渡江是「古代打仗比较不太道德，突破底线」；发言人1补充吕蒙因此被后世与「小偷鼠辈」画等号，二人一致。对《红楼梦》后四十回，发言人4认为高鹗续写版本「总体来说还是比较合理」，官方说法「没有违背作者原意」；发言人2则对续写结局表示「没看明白他到底是想说啥」，对合理性存疑，双方未就此达成统一。
+# 待探讨问题与后续
+- **未确认：** 红楼梦后四十回是否为高鹗续写及其官方定本地位，发言人2对高鹗续本为何成为官方结尾提出疑问，发言人4回应称官方说法是依据残稿梳理完善、未违背作者原意，但发言人2仍表示「没看明白他到底是想说啥」。
+- **未定论：** 探春、史湘云等人物结局仅凭判词无法明确，发言人4指出「都是猜的」，未有人能确切说出最终谁与贾宝玉在一起。
+- **未确认：** 红楼梦存在「反清复明」版本解读，发言人2提及林黛玉、薛宝钗分别代表明朝与清朝的说法，发言人4补充秦可卿被解读为前朝公主，均属民间解读、未获证实。
+- **待核实：** 北京植物园附近存在「曹雪芹小道」，发言人3称在北苑所旁边村子爬山时见过，发言人2提及植物园内有曹雪芹故居，具体位置与史实依据未进一步核实。
+- **未定论：** 三国部分对刘备称汉中王是否引发孙刘决裂存在不同看法，发言人1认为称王不妥引发连锁反应，发言人2未明确表态，仅表示受演义影响偏好蜀汉阵营。</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6453/2967</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="13.5" customHeight="1" s="9">
       <c r="A51" s="6" t="inlineStr">
@@ -15677,6 +16863,54 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论由发言人1发起，延续此前《红楼梦》《三国》《水浒》《西游记》《金瓶梅》的系列话题，从兵法和战法角度切入三国战役。成员共3人，按原文编号为发言人1、发言人2、发言人3。讨论围绕赤壁之战与合肥之战的影响、火烧连营与陆逊评价、孙权军事能力与蜀汉武将评价三大议题展开。发言人1系统分析了曹操因以骑兵为主、缺乏水军而败于赤壁，东吴北伐必经合肥而孙权一生未能攻克，并详述公元215年合肥之战中张辽率800死士大败孙权十万大军的过程；随后讲述刘备在夷陵之战因体恤下属在密林扎营，被陆逊抓住秋季干燥时机火攻、连营七百里被烧的经过。发言人2对孙权评价表示前后反差，发言人3补充孙权早期败仗及蜀汉武将看法。整体以分享观点为主，未形成统一结论，对孙权军事能力评价偏负面，对关羽战力认可度较高。讨论按议题逐块推进，由发言人1主导讲述，其余成员补充与回应，并延伸至北伐路线与街亭之战假设。
+# 发言要点
+## 赤壁之战与合肥之战的影响
+- **发言人1**：赤壁之战曹操失败主因是军队以虎豹骑等骑兵为主、擅长陆战，刚收服荆州没有像样水军，面对长江如同渡海攻坚战，过不去长江；东吴则以水军为主，双方各有所长。
+- **发言人1**：东吴北伐必经合肥——从建业（今南京）过长江到江北，经小河到巢湖上岸，打下合肥后才能靠近淮河，再连徐州、鲁西南乃至海河一带；孙权一生多次攻合肥均未攻克。
+- **发言人1**：公元215年合肥之战，曹军主力在攻汉中，合肥仅张辽、李典、乐进三将镇守且三人矛盾深（张辽原属吕布）；张辽率800死士骑马冲阵，大败孙权十万大军，留下「张八百大破孙十万」的段子。
+- **发言人1**：合肥之战中孙权在城外扎营准备攻城，张辽突袭时吴军未及反应；张辽战后询问俘虏，得知骑术好、箭法准、上身长下身短、留小胡子的逃跑者就是孙权，后悔差点将其擒获。
+- **发言人1**：合肥城内张辽跺两脚连小孩都不敢啼哭；后人吐槽孙权「正面打不过、偷盟友家专业」，南京紫金山孙权墓确切位置已失，碑前堆满张辽的影视海报和游戏卡片。
+- **发言人2**：小时候看「生子当如孙仲谋」觉得孙权厉害，长大后观感反转，认为其评价偏负面。
+- **发言人3**：孙权在孙十万之前也打过败仗，几万人被对方几千人追着打，对手可能是刘繇或类似人物，但具体是谁记不清。
+- **发言人1**：曹操说「生子当如孙仲谋」是因为孙策传位给孙权，孙权开疆拓土不行但能守住家业，对比曹操诸子算争气的。
+## 火烧连营与陆逊评价
+- **发言人1**：夷陵之战刘备体恤下属，不忍酷暑折磨让士兵在密林扎营避暑；陆逊抓住秋季干燥、树叶飘落的时机放火，连营七百里被烧光，刘备只身逃回白帝城。
+- **发言人2**：问陆逊是否与孙家有仇，陆家和孙家没听过有仇。
+- **发言人1**：陆逊是江东四杰之一；孙策因是外来户、行事冒失被称为「小霸王」，后被刺杀。
+## 孙权军事能力与蜀汉武将评价
+- **发言人3**：从南往北打的成功案例除朱元璋外不好找，多数能守住首都就不错，暗指南北作战方向差异。
+- **发言人1**：夷陵之战刘备被仇恨冲昏头脑而冒进；汉中之战有法正、黄权辅佐，靠地势地利把曹操耗出汉中，打得还行。
+- **发言人1**：论打仗关羽很厉害，水淹七军之外还有阵中斩将——斩颜良、诛文丑，是历史上第一个阵中斩将直接改变战场局势的人。
+- **发言人3**：关羽个人战力强，但水淹七军之外想不起其他部队作战战绩。
+- **发言人1**：黄忠定军山阵斩夏侯渊，但可能与关羽不同，关羽是摆好阵后斩将，黄忠像是从山上冲下来。
+- **发言人3**：张飞想不起经典战役，只知道长坂坡。
+- **发言人1**：演义里张飞与马超在成都城下大战五百回合。
+- **发言人3**：正式打仗列阵交锋方面，五子良将（张辽、曹仁、夏侯渊、张郃、徐晃、于禁）战力受认可，张辽是从吕布降过来的。
+- **发言人1**：曹操兵多血厚耗得起；若诸葛亮第一次北伐用魏延守街亭，大概率能反杀张郃，不会像马谡那样轻易丢掉街亭，北伐可能成功；但魏延想法大胆，不符合蜀汉实际支撑。
+- **发言人3**：蜀汉地盘太小，支撑不起魏延的冒险打法。
+# 共识形成
+- **一致意见**：赤壁之战与合肥之战均体现水军与骑兵的作战差异——曹操因以骑兵为主、缺乏水军而败于赤壁；东吴北伐必经合肥，孙权一生未能攻克，公元215年合肥之战中张辽率800死士大败孙权十万大军，孙权本人险被俘虏。与会者认同孙权军事能力评价偏负面，认为其守成有余、开疆不足。
+- **倾向性认识**：对蜀汉武将战力，发言人1与发言人3倾向认可关羽，认为其有阵中斩将战绩（斩颜良、诛文丑），黄忠定军山阵斩夏侯渊亦获认可；张飞缺乏经典战役，仅知长坂坡。发言人1提出若魏延守街亭可能反杀张郃，但魏延想法不符合蜀汉实际，发言人3以「地盘太小了」表示认同。
+- **主要分歧点**：发言人3提及孙权在孙策刚死时曾以数万人被几千人追打，但具体对手与战役名称未能确认，发言人1先后猜测刘表、张辽、曹仁、刘琦等均被发言人3否定，该战役细节未定论。
+# 待探讨问题与后续
+- **未确认**：发言人3提到的孙权早期败仗的具体对手和战役未确认，其仅描述为「孙策刚死的时候」、对手「不是刘表」、在张辽之前，发言人1先后猜测「刘琦时期」「曹仁时期」均未获确认。
+- **未定论**：关于关羽阵中斩将是否为「历史第一人做到」的讨论未达成定论，发言人3提出此说法，发言人1以黄忠定军山阵斩夏侯渊作对比，发言人3认为两者情况不同（关羽为摆好阵后斩将，黄忠可能为从山上冲下），但未进一步核实。
+- **未定论**：若诸葛亮第一次北伐时以魏延守街亭能否反杀张郃、北伐能否成功，仅为发言人1的假设性判断，发言人3仅回应「这地盘太小了」，未展开讨论。
+- **未确认**：发言人3提及孙权早期另有一场「几万人被几千人追着打」的败仗，但对手姓名（「刘油」「刘有」等）始终未能回忆确认。</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4899/2473</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="13.5" customHeight="1" s="9">
       <c r="A52" s="6" t="inlineStr">
@@ -15732,6 +16966,74 @@
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次专项讨论会由主讲人（原文未提及姓名）讲解苏阿战争（1979—1989年苏联入侵阿富汗战争）的背景、经过与结果，形式为专题讲解加听众提问。讲座面向对冷战史与地缘政治感兴趣的听众，旨在说明阿富汗的战略地位与“帝国坟场”成因。内容围绕四个板块展开：阿富汗地理与历史背景、苏联出兵经过、各方援助与游击战、苏联撤军原因。核心判断有三：其一，阿富汗地处亚洲中间走廊，谁控制阿富汗谁就控制亚洲咽喉；其二，其国土90%为高原山地、乡村由部落长老制控制，使外部力量难以有效统治；其三，苏联出兵阿富汗属战略性失误，最终被人民战争消耗至撤军。关键锚点包括1979年12月24日平安夜苏联突袭喀布尔、1989年苏联撤军、美国援助“毒刺”防空导弹压制苏军武装直升机。对听众而言，本讲有助于理解冷战格局下大国干预的代价及阿富汗问题的历史根源。
+# 核心观点与论证
+## 阿富汗是亚洲咽喉与帝国坟场
+- **地理位置**：阿富汗东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，是兵家必争之地。
+- **地形特征**：国土90%为高原山地地带，易守难攻，是天然的游击战地区，历史上多次获得帝国坟场称号。
+- **控制意义**：谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+- **资源状况**：阿富汗是贫油国，但周边国家如西边的伊朗、北边的土库曼斯坦和塔吉克斯坦都是富油国。
+## 苏联出兵阿富汗的背景与经过
+- **战前态势**：20世纪50年代，阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，国内精英阶层奉行亲英与亲苏两头政策，文化上师从英国，国家建设和工业方面向苏联看齐。
+- **阿明转向**：基辛格评价阿明是用的苏联的火柴点美国的香烟，阿明对苏联日益干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前武力介入。
+- **入侵过程**：1979年12月24日平安夜，苏联以阿富汗请求救援的说法，从东部、中部及西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一个晚上控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台。
+- **国际反应**：众多阿拉伯国家、中国和西方盟国共同不满抵触，合力援助阿富汗，由阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源，支持阿富汗抵抗组织进行长达十年的游击战争。
+## 苏联出兵是战略性失误
+- **勃列日涅夫逻辑**：阿富汗被苏联化为苏联大家庭中的一员，根据勃列日涅夫逻辑不允许任何成员外出，类似之前出兵捷克，阿富汗是必须要下场的。
+- **冷战背景**：同时期处于苏攻美守时期，苏联咄咄逼人进行意识形态扩张及军事霸权恐吓，共同导致苏联出兵阿富汗。
+- **战略错判**：阿富汗是非常特殊的战略要地，加上苏联的错判，导致苏联大大的战略性失误。
+## 阿富汗难以被外部力量控制
+- **部落结构**：除喀布尔和坎大哈等主要城市外，90%地区为乡村部落长老制，政府没有任何控制力，各村落与部落各自为政，任何列强及城市政府无法对高原山地形成有力控制。
+- **中国援助**：中国帮助阿富汗圣战抵抗者，教授抗战时期的地道战、地雷战等战法，与苏联持续进行游击战争。
+- **美国援助**：美国援助了先进的单兵武器毒刺防空导弹（类似火箭筒），可有效压制苏联最先进的雌鹿武装直升机。
+- **苏军困境**：坦克和步兵战车在阿富汗无法形成有效战斗力，因这些装备主要用于平原地带，高原山地需步兵加武装直升机才能有效作战；苏联军事实力看似庞大但武器发挥不了作用，基层官兵普遍厌战，士气一落千丈，最终1989年撤军。
+## 圣战者的作战思想
+- **思想特征**：圣战者具备狂烈激进的伊斯兰圣战思想，以及从上到下宗教式洗脑，导致其像二战时期日本军国主义荼毒下的日本军民一样，抱着同归于尽的思想进行圣战。
+## 中国对阿富汗的援助方式
+- **武器援助**：中国提供了与AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助形式将已饱和的军工业产业稀释掉。
+- **合作默契**：中国与西方盟国为抵抗苏联霸权主义达成秘而不宣的默契。
+- **人员派遣**：中国只提供军火和兵法指导，派专家教授地道战、地雷战，但未派人参战。
+# 金句总结
+&gt; 谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+- 回答听众关于阿富汗为何被多国争夺的提问，点明其地理位置的关键性。
+&gt; 阿富汗多次获得其帝国坟场的称号。
+- 讲述阿富汗历史时，概括列强入侵屡遭失败的结局。
+&gt; 基辛格评价阿富汗当时的国王阿明，说是用的苏联的火柴在点的美国的香烟。
+- 描述阿富汗在美苏之间两头要好处、左右逢源的处境。
+&gt; 苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。
+- 分析苏联重装部队在阿富汗高原山地无法有效作战、最终撤军的原因。
+&gt; 苏军的士气也是一落千丈。
+- 说明苏联基层官兵普遍厌战、不明白为何而战，导致战斗力与士气崩溃。
+&gt; 咱们国家当时也是帮助那个阿富汗圣战抵抗者，教他们兵法，就比如说咱们以前抗战时期所用的，比如地道战、地雷战这样的一个战法。
+- 介绍中国对阿富汗抵抗组织的援助方式，即提供兵法指导而未直接派兵。
+# Q&amp;A 环节
+**听众**：阿富汗到底有啥好呀？为啥都想打它？
+**主讲人**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+**听众**：是不是阿富汗有石油啊？
+**主讲人**：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
+**听众**：其实这个我感觉得用当时的冷战思维来看，因为阿富汗当时被苏联化为苏联势力、苏联大家庭中的一员。根据勃列日涅夫的逻辑，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，加上苏联这个错判，导致苏联大大的战略性失误。
+**主讲人**：对的，同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人地进行意识形态的扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
+**听众**：之前看那个阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
+**主讲人**：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民那样，不顾一切地抱着同归于尽的思想进行圣战。
+**听众**：其实这次苏阿战争之前，已经有三次英阿战争，阿富汗被称为帝国坟场，可以简单说一下为什么这个位置这么难打？虽然它的国土面积没有那么大，经济实力又没有那么好。
+**主讲人**：因为这个国家百分之九十都是处于高原山地地带，是一个天然的游击战地区。除了喀布尔和坎大哈那几个主要城市以外，剩下大部分百分之九十的地区都是乡村部落长老制，政府没有任何控制力，由部落长老控制，各个村落与部落各自为政，导致任何列强以及阿富汗的城市政府都无法对广大的高原山地形成有力控制。同时期咱们国家帮助阿富汗圣战抵抗者，教他们抗战时期所用的地道战、地雷战等战法，和苏联持续进行游击战争；美国也援助了比较先进的单兵武器，比如毒刺防空导弹，可以有效压制苏联最先进的武装直升机雌鹿。坦克和步兵战车在阿富汗无法形成有效战斗力，因为这些装备主要用于平原地带，在高原山地还是要以步兵加武装直升机才能形成有效战斗力。苏联军事实力看似庞大，但武器发挥不了作用，基层官兵普遍厌战，士气一落千丈，最终1989年扛不住压力撤军。
+**听众**：咱们男生基本都说完了，都说过一遍了。
+**主讲人**：也是给了一些枪炮，比如咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助的形式把咱们国家已经饱和的军工业产业稀释掉，同时大家为了抵抗苏联霸权主义和西方盟国达成了一种秘而不宣的默契。
+**听众**：只提供军火，但是没有派人。
+**主讲人**：专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3129/3290</t>
         </is>
       </c>
     </row>
@@ -15921,6 +17223,69 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论由4位发言人（发言人1、发言人2、发言人3、发言人4）围绕各国文学特点展开漫谈式分享，由《白夜行》的悬疑叙事与阴暗结局切入，借《菊与刀》引出对日本民族性格的观察，随后依次比较法国、英国、俄国、美国文学在底层描写、抗争精神与理想主义上的差异，并延伸至中国底层文学的政策限制、台湾电影《假如我是真的》与上山下乡历史背景、苏联时期作家作品，最后以《西游记》狮驼岭章节的黑暗解读收束。讨论以分享观点为主，未形成统一结论，整体按议题逐块推进，从日本文学出发，经多国文学比较，再转入历史社会背景与具体作品解读，发言间相互补充与引申。
+# 发言要点
+## 日本文学《白夜行》讨论
+- **发言人1**：《白夜行》是悬疑小说，叙事手法独特，上来都是隐藏信息，让人一直猜不到真相，每个人都有嫌疑，但结局非常阴暗。
+- **发言人2**：美国作家本尼迪克特《菊与刀》生动描绘了日本人性格特点，《白夜行》也能体现这一点，并由此引出各国文学偏好话题。
+## 各国文学特点比较
+- **发言人2**：法国文学体现浪漫的理想主义精神和奉献，尤其在《悲惨世界》中生动体现。
+- **发言人4**：法国相对英国小说，描绘底层民众更多一些，英国的多是贵族生活。
+- **发言人1**：法国挺爱革命，有抗争精神；英国想维持他们那套，法国确实革命了好多。
+- **发言人2**：英国后期土地承载不了人口膨胀，以英国、爱尔兰为主带头移民北美新大陆，这是根本原因。
+- **发言人1**：英国像《圣诞欢歌》《雾都孤儿》也讲底层，写贵族和穷人之间有鸿沟，穷人把希望寄托在宗教或虚无的东西上。
+- **发言人2**：美国历史短，叙事风格不同于欧洲，更多表现在现代社会，与欧洲理想主义的精神图腾不太一样。
+- **发言人1**：美国历史太少，美洲大陆没发生欧亚大陆那么多悲惨事情，相对还是幸福的，如《了不起的盖茨比》。
+- **发言人2**：北美大平原农业资源广阔，美国今天经济不好也永远不缺粮食；欧亚大陆的瘟疫、大饥荒在美国从未发生过，美国人无法真正理解饥荒为何物。
+- **发言人1**：电影《一九四二》讲的就是大饥荒和战乱。
+- **发言人2**：日本人能打垮国民党军队，是因为给灾民发放粮食，而国民党对灾区视而不见，结果日本人占领了河南省大部地区。
+- **发言人1**：有人打仗给日本人报情报换取粮食，这是人性，没办法。
+## 中国底层文学与历史背景
+- **发言人1**：国内写底层的其实写得很深刻，像《平凡的世界》，但好多因政策原因不让看了，以前很多根据底层小说改编的电影也不让看。
+- **发言人2**：台湾电影《假如我是真的》改编自俄国果戈里《钦差大臣》，结合文革知青上山下乡真实事件，上世纪七十年代末、八十年代初拍摄。
+- **发言人2**：当时台湾和大陆搞舆论宣传战、意识形态攻略，台湾把大陆上山下乡、文革时期的不公通过电影批判出来。
+- **发言人1**：他们批判自己，也批判平衡，台湾总会拍电影。
+## 俄国文学与苏联时期作品
+- **发言人2**：个人比较喜欢契诃夫，如《变色龙》《装在套子里的人》《凡卡》。
+- **发言人2**：苏联时期喜欢格罗斯曼，他是红军战地记者，写了《命运与生活》，以小说方式出版红军后期进入欧洲后看似不公的问题，从平民视角看苏联红军的基层真实形象。
+- **发言人2**：《古拉格群岛》真正把人性黑暗面批判出来，最早出版版本是法语版，俄语版要等苏联解体后才发行。
+- **发言人2**：俄国文豪如列夫·托尔斯泰是前线俄军，把老百姓疾苦、不公与贵族奢华对比讽刺；因沙俄新闻管制严厉，以小说方式发表。
+- **发言人2**：俄国文学与法国文学有相似也有不同，对人性丑恶的揭露与批判更为讽刺，《古拉格群岛》和契诃夫作品都是表现。
+- **发言人2**：高尔基《海燕》是老百姓被压迫久了之后的呐喊和挣扎，是走投无路后奋起的反抗。
+- **发言人1**：苏联时期作者挺多，但看得很少，反倒是高尔基因为正面宣传看得比较多。
+- **发言人1**：初中高中时有英语读物要求中英对照读名著，自己不看英语只看汉语，觉得挺有意思。
+## 《西游记》狮驼岭章节解读
+- **发言人2**：狮驼岭章节生动揭露佛教世界的虚伪，佛门三大圣兽青狮、白象和大鹏偷下界，把城池所有人吃掉，扶植小妖成为国家公民。
+- **发言人2**：唐僧师徒路过时满国尸骸遍地，孙悟空都不战而弃、发抖；原著描写人皮当地毯、骷髅头骨当装饰物和器具，此地距离灵山不过500公里左右。
+- **发言人2**：这与佛门所说普度众生、众生平等大相径庭；旧社会西藏王公大臣就是这种状态，共产党没解放西藏悲剧会延续到今天。
+- **发言人2**：吴承恩在古代就预测并批判揭露佛教在部分地区是上层王公大臣迷惑底层民众、高压奴役的统治工具，这是汉传佛教和藏传佛教截然不同的本质。
+- **发言人4**：问狮驼岭是啥，这个是不是没有拍到电视剧。
+- **发言人2**：有拍，但没把那些惨案讲得那么生动，最后佛祖出手收回，孙悟空终究要被大鹏精打败，大鹏精是全书唯一能遛猴子的反派。
+- **发言人1**：电视剧就拍几个妖精是大王，过去全给干了；黑神话悟空也没设计那一章，太血腥不好过审，而且意义深刻，剧情既要委婉又要深刻很难。
+# 共识形成
+- **一致意见**：与会者普遍认同《白夜行》叙事手法独特、结局阴暗，并认可《菊与刀》对日本人性格特点的描绘；在各国文学比较中，**法国文学体现抗争精神与浪漫理想主义（如《悲惨世界》）**、英国文学多描写贵族生活、俄国文学对底层民众的描绘更生动且对人性丑恶的揭露与批判更为讽刺（如契诃夫、托尔斯泰、《古拉格群岛》）、美国文学历史短且多表现现代社会，这些判断得到多人呼应。
+- **倾向性认识**：发言人1与发言人4认为法国文学比英国文学更侧重描绘底层民众，英国文学多写贵族生活；发言人2补充法国文学具有浪漫理想主义精神与奉献色彩。发言人2认为俄国文学在底层描写上比法国更生动，发言人4回应俄国文学戏剧性更明显、更曲折。
+- **主要分歧点**：在底层文学受限问题上，发言人1主张国内底层文学（如《平凡的世界》）因政策原因受限，发言人2则以台湾电影《假如我是真的》为例，指出其结合俄国《钦差大臣》与文革知青上山下乡事件，是台湾对大陆舆论宣传战的产物——两人对国内底层文学受限原因的判断口径不一致（政策限制 vs 两岸舆论对抗背景）。在《西游记》狮驼岭解读上，发言人2认为该章节批判佛教被上层利用、汉传与藏传佛教本质不同，发言人1与发言人4未直接反驳，但仅就电视剧与游戏未充分展现该章节黑暗内容（人皮地毯、骷髅装饰等）表示认同，未对发言人2的宗教批判结论表态。
+# 待探讨问题与后续
+- **未确认**：发言人1提到国内底层文学（如《平凡的世界》）「因政策原因不让你看了」，但未说明具体政策依据或哪些作品受限，此说法仅为个人观点，未获其他成员证实或展开。
+- **待核实**：发言人2称《古拉格群岛》「最早出版的版本还是法语版的，俄语版的还要等到苏联解体之后才发行」，此版本时间线未在讨论中进一步核实。
+- **未确认**：发言人2称台湾电影《假如我是真的》「改编自俄国小说《钦差大臣》并结合文革知青上山下乡事件」，发言人3当场追问「他讲的是啥呀」，发言人2以「先不剧透」回避，影片具体情节与改编关系未展开说明。
+- **未定论**：发言人2认为《西游记》狮驼岭章节中吴承恩批判佛教被上层利用、汉传佛教与藏传佛教「本质截然不同」，此解读为发言人2个人观点，其他成员未表示认同或反对，也未就此达成一致。
+- **未确认**：发言人2称狮驼岭章节「此地距离灵山也不过500公里左右」，并以此类比西藏与菩提迦耶的距离，该地理数据未在讨论中核实。
+- **未定论**：发言人1提到《黑神话：悟空》未设计狮驼岭章节，推测「不太好过审」「太血腥」，但未确认游戏方是否确有相关设计或删减安排，仅为猜测。</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5886/3302</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="13.5" customHeight="1" s="9">
       <c r="A54" s="7" t="inlineStr">
@@ -15986,6 +17351,87 @@
       <c r="B54" s="7" t="inlineStr">
         <is>
           <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次例会由产品经理主持，产品、开发1、开发2参与，围绕手机图库项目进展，对齐了智能分类与相册推荐改版、AI智能标签接口、同步模块、缩略图渲染、时间轴加载优化、AI修图预留及里程碑计划等议题。产品侧汇报高保真原型V1.5版已出，用户调研反馈隐私相册入口太深，产品经理同意将入口提升至首部顶部二级菜单并要求出交互方案评审。开发侧同步多项技术进展：AI标签V2模型准确率提升约88%，但单次请求耗时从800毫秒增至约1.5秒，决定采用本地缓存策略并采纳端侧预过滤方案；同步模块因队列积压超1000张导致部分机型OOM崩溃，维持分片加载方案；缩略图渲染改用新解码库，内存占用降约30%，主流机型帧率稳定60帧；时间轴采用本地索引预加载方案。AI修图本次不实现，预留接口和插件化架构。里程碑按原定计划月底封版，内测包暂定下周三发。
+# 分段速览
+## 00:00:00-00:01:23 开场与产品侧进展
+产品经理开场说明会议目的：过手机图库项目整体进展，对齐排期与潜在风险，按产品侧、开发侧、总结的顺序进行。产品侧汇报近两周重点推进智能分类和相册推荐改版，高保真原型已出V1.5版，调整了网格视图交互逻辑和长按微动效反馈。测试反馈低端机上滑列表偶尔掉帧，已与开发2沟通，拟通过降低预览图缩放级别换取帧率。用户调研收到不少关于隐私相册入口太深的吐槽，建议下一版将入口提到首部顶部二级菜单。产品经理回应：隐私相册入口提升不算大改动，同意推进并要求出交互方案评审；掉帧问题需抓紧，下周将进入性能压测。
+## 00:01:51-00:03:19 AI标签接口与同步模块问题
+开发1汇报AI智能标签接口进展：V2版识别模型已跑通，准确率较上一代提升约88%，但因新增视频帧提取功能，单次请求耗时从800毫秒涨至约1.5秒，需产品侧评估用户接受度，备选方案是改异步推送。产品反对异步推送，认为用户点开相册无实时结果会感觉功能卡死，提出先做本地缓存策略——首次识别慢、之后本地读库秒出。开发1确认可行，计划下午拉分支改逻辑，预计三天联调完，但提示缓存命中率低时仍需回溯。开发1同时提出云相册同步模块断点续传在弱网环境下出现状态机紊乱。开发2反馈同步队列积压超1000张时部分机型出现OOM崩溃，iOS尤其严重，已采用分片加载机制每次拉50张，但会拖慢同步进度，需与产品商量是否加后台静默同步权限或允许用户手动设置同步频率。
+## 00:03:57-00:05:03 同步方案与缩略图渲染优化
+产品经理指出后台同步权限审核严、大概率下不了，决定维持分片加载方案但进度不能拖。开发2汇报缩略图渲染优化：改用新图片解码库，将JPEG硬解换为软解，内存占用降约30%但CPU占用上升；已在主流三款机型灰度，帧率稳定60帧、低端机约50帧，周四性能报告今晚可出初稿。另提出批量删除照片时若同时触发回收站重建索引，数据库偶尔锁死，已用消息队列排队处理作临时规避，正式修复预计排到下下周版本。产品经理决定临时规避先稳住，正式修复排进V1.2迭代。
+## 00:05:35-00:07:25 端侧预过滤与时间轴加载优化
+产品经理提出端侧预过滤思路：先用轻量级模型扫一遍，过滤明显非图片的gif或截图，剩余再走全量云端识别，预计可将平均耗时压下一半。开发1认可该思路，将评估模型体积和端侧推理开销，若放端侧跑需再申请200兆本地缓存空间，请产品评估对安装包体积的影响。产品回应安装包加两三百兆问题不大，建议做成按需加载——用户首次进图库智能标签时才触发下载，平时不占空间，开发1确认可用现有资源下发模块实现，约两天搞定，并拉开发2配合端侧推理联调。开发1另提出时间轴视图加载问题：测试提了三个优高优Bug，滑动到二十年前老照片时页面卡死三秒以上，原因是历史图片EXIF解析耗时加磁盘IO瓶颈，准备加本地索引预加载，最近三个月照片建树状结构、滑到底部动态加载旧数据。产品经理同意改动，但提醒注意别与云同步模块抢资源。开发2确认不会冲突——预加载放主线程IO池、同步放子线程后台服务，但预加载需用户授权媒体和存储权限，若首次拒绝需引导弹窗，弹窗交互由产品设计。
+## 00:07:48-00:09:42 AI修图预留与管线重构
+产品提出运营希望下版本加AI修图快捷入口（一键去背景、智能调色），本次排期可能塞不进去，想提前占坑、架构上留好接口。产品经理决定本次主线是性能和分类，不硬塞AI修图，在PRD里先写好接口逻辑和UI占位，开发侧把模块抽象成插件化架构，下次迭代直接接入；后端接口按标准RESTful加Swagger文档输出。开发1确认微服务架构下按规范出文档很轻松，同时指出端侧若预留AI修图渲染通道，需重构当前耦合较深的图片处理管线。开发2表示近期也在考虑管线优化——现在每加滤镜就得改底层代码，拟将渲染层抽成插件化、用GLSL写统一接口，工作量约多一周，需产品经理确认能否把非核心Bug修复往后挪。产品经理同意调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化，要求开发2今天下班前评估精确工作量，开发1排联调时间、尽量周五前跑通主干流程。
+## 00:10:19-00:12:18 里程碑与内测安排
+产品确认下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查，同时制作AI修图占位图保持视觉一致性，并询问项目里程碑与内测包时间。产品经理确认里程碑按原定计划月底封版，内测包暂定下周三发，届时拉体验官群重点跑AI分类和同步模块，产品准备反馈收集表、开发准备日志抓取。开发1提出需与数据库组对齐索引策略，产品经理同意拉群让DBA配合优化建表。开发2确认今晚继续跑分片加载和渲染优化压测数据，并询问周四性能评审是否将iOS和安卓对比数据单独列版，产品经理同意分开列、由测试组合并为一份总览。产品经理下午两点参加UI走查，产品承诺十一点半前发稿。会议结束。
+# 要点梳理
+## 智能分类与相册推荐改版
+- **高保真原型**：已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈
+- **低端机掉帧**：测试反馈上滑列表偶尔掉帧，计划通过降低预览图缩放级别改善，已与开发2沟通
+- **隐私相册入口**：用户调研反馈入口太深，建议下一版提升至首部顶部二级菜单；产品经理同意，不算大改动，要求出交互方案评审
+## AI智能标签接口与性能
+- **模型升级**：V2识别模型已跑通，准确率较上一代提升约88%
+- **耗时问题**：新增视频帧提取功能后，单次请求耗时从800毫秒增至约1.5秒
+- **异步推送方案**：产品明确反对，认为用户点开相册无实时结果会感觉功能卡死
+- **本地缓存策略**：采用首次识别慢、之后本地读库秒出的方案；开发1下午拉分支改逻辑，预计三天联调完；缓存命中率低时仍需回溯
+- **端侧预过滤**：先用轻量级模型过滤gif或截图，再走云端识别，预计平均压一半耗时；需评估模型体积和端侧推理开销，可能申请200兆本地缓存空间
+- **按需加载**：用户首次进智能标签时才触发下载，平时不占空间；用现有资源下发模块即可，预计两天完成
+## 同步模块与内存管理
+- **OOM崩溃**：同步队列积压超1000张时部分机型崩溃，iOS内存回收机制激进尤其严重
+- **分片加载**：已实施每次拉50张、处理完再拉下一批的机制，但会拖慢同步进度
+- **后台同步权限**：审核严，大概率无法申请；决定维持分片加载方案，但进度不能拖
+## 缩略图渲染与性能优化
+- **解码库优化**：JPEG硬解换软解，内存占用降约30%，CPU占用上升
+- **灰度测试**：主流三款机型帧率稳定60帧，低端机约50帧；周四性能报告初稿今晚出
+- **数据库锁死Bug**：批量删除照片同时触发回收站重建索引时偶发锁死，已用消息队列排队临时规避；正式修复排进V1.2迭代
+## 时间轴视图加载优化
+- **卡死问题**：滑动到二十年前老照片时页面卡死三秒以上，测试提了三个优高优Bug
+- **根因**：历史图片EXIF解析耗时过长，叠加磁盘IO瓶颈
+- **预加载方案**：最近三个月照片建树状结构，滑到底部动态加载旧数据；需与云同步模块隔离资源
+- **权限引导**：预加载需用户授权媒体和存储权限，拒绝时需引导弹窗；产品明天出稿，走柔和提示路线
+## AI修图功能预留
+- **需求来源**：运营反馈希望下版本加AI修图快捷入口（一键去背景、智能调色）
+- **本次范围**：不硬塞进当前迭代，主线为性能和分类；在PRD中预留接口逻辑和UI占位
+- **插件化架构**：开发侧将模块抽象，端侧重构图片处理管线，用GLSL写统一接口；工作量约多一周
+- **后端接口**：按标准RESTful加Swagger文档，便于后续迭代对接
+## 结论与决定
+- **隐私相册入口**：提升至首部顶部二级菜单，产品出交互方案评审
+- **AI标签方案**：采用本地缓存策略加端侧预过滤，按需加载；开发1与开发2配合联调
+- **同步模块**：维持分片加载方案，每次拉50张，进度不能拖
+- **缩略图渲染**：采用新解码库优化，临时规避方案先稳住，正式修复排进V1.2
+- **时间轴优化**：采用本地索引预加载，注意与云同步模块资源隔离
+- **AI修图**：本次不实现，预留接口和插件化架构，非核心Bug修复往后排
+- **里程碑**：按原定计划月底封版，内测包暂定下周三发
+## 行动项与分工
+- **发言人2（产品）**：下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查；制作AI修图占位图；准备反馈收集表；十一点半前将UI稿发给产品经理
+- **发言人3（开发1）**：下午拉分支改本地缓存逻辑，预计三天联调完；评估端侧预过滤模型体积和推理开销；按需加载预计两天完成；拉开发2配合端侧推理联调；今晚搭好接口联调环境，明天与测试过一遍；拉群与DBA对齐索引策略
+- **发言人4（开发2）**：今晚继续跑分片加载和渲染优化压测数据，明天同步；评估AI修图管线重构工作量，今天下班前发给产品经理
+- **产品经理**：周四参加UI走查；要求测试组将iOS和安卓性能报告合并为一份总览；调整非核心Bug优先级，资源给到管线重构和AI标签优化
+## 待确认与风险
+- **端侧预过滤**：模型体积和端侧推理开销待评估；需申请200兆本地缓存空间，对安装包体积的影响待产品评估
+- **AI修图插件化**：具体实现方案待开发2评估工作量
+- **权限引导弹窗**：交互设计待产品出稿
+- **低端机掉帧**：上滑列表掉帧影响用户体验
+- **AI标签耗时**：单次请求从800毫秒涨至1.5秒，可能影响用户等待体验
+- **OOM崩溃**：同步队列积压超1000张时部分机型崩溃，iOS尤其严重
+- **数据库锁死**：批量删除照片时偶发，影响数据一致性
+- **时间轴卡死**：滑动到老照片卡死三秒以上，影响核心功能体验
+- **权限拒绝风险**：预加载需用户授权，若拒绝可能影响功能使用
+- **后台同步权限**：审核严，可能无法申请</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3605/4587</t>
         </is>
       </c>
     </row>
@@ -16069,6 +17515,92 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次月度研讨会由总监主持，组长、销冠、销售A、销售B共同参与，围绕上月销售数据复盘与下月去化目标制定展开。会议覆盖销售数据复盘、工地开放日标准化、逼定策略、渠道带看管控、老带新政策、目标分解、专项培训及销控纪律等议题。核心结论为量够但转化不足，需重点提升逼定和转化环节，并明确下月总去化目标120套、工地开放日每周三固定开放、渠道带看实名制、周末业主答谢会联动去化等关键决定。上月案场总到访320组、成交76套、转化率23%，下月目标较上月增加50%。
+# 分段速览
+## 00:00:00-00:01:17 开场与整体数据复盘
+总监宣布月度研讨会定于下午两点至两点四十，共四十分钟，指出上月市场波动大、项目整体去化尚可但部分数据不理想，要求组长先过核心指标。组长汇报后台完整数据：上月案场总到访三百二十组，环比增加百分之十五，数据达标；但成交七十六套，转化率百分之二十三，较上月百分之二十七下降四个百分点；渠道带看占比百分之六十五，自然来访仅百分之三十五；蓄客量约三千二百组，认购到成交流失率约百分之十八。总监总结为量够但卡在逼定和转化环节，并指出渠道带看比例过高意味着自主拓客和案场拦截能力在退化。
+## 00:01:53-00:03:36 客户流失抗性分析与工地开放日建议
+销冠复盘上月流失客户，集中在两个抗性：价格预期方面竞品推特价房、首付分期或送物业费，客户有心理落差；交付信心方面客户对园林选材、地下车库层高、外墙保温层等细节询问细致，怕买错，建议把工地实时进展和材料样板直接呈现。销售A分享改善型客户案例，带看三次并让客户直接问施工经理，客户因工程透明才定房，但工地开放日频率不够、陪看占时间影响转化。组长建议设固定节点，每周三下午固定开放，提前在客户群和朋友圈发预告，客户直接对接专属顾问。总监认可并要求组长出方案，定每周三、提前两天在CRM系统推送意向客户。
+## 00:04:22-00:06:12 逼定策略与物料更新
+销冠分享逼定手法：不直接降价，而是算总账，将物业费、车位管理费、未来装修损耗拉表对比竞品，强调单价虽高两千但十年省下物业和品质维修维护费，再递上“限时权益”逼定函，承诺本周定下来亲自申请多送三年物业费，客户怕错过、看重确定性。销售B指出客户对“限时权益”不买账，需将权益具象化，如把三年缴费明细打印放在合同旁；同时反映案场物料更新慢，逼定函常是上月版本。组长记录物料问题，联系设计本周出新版，把权益条款写清楚，并计划下月制作“权益可视化”台卡放在洽谈区；同时指出跟进节奏慢，客户晚上问政策回复慢热度下降。
+## 00:06:12-00:08:27 跟进提速与渠道管控
+总监强调客户不过夜，要求分片包干：组长带销售A和销售B回访上周未成交的三百多组，重点盯“再考虑考虑”的客户；销冠梳理手头二十几个高意向客户，看能否周末逼定。针对渠道无效带看多、中介随便拉人凑数的问题，总监要求下月起带看必须实名登记并有明确需求标签，否则扣减渠道积分。销售A反映中介抵触，担心渠道不愿推盘，总监表示渠道部由他沟通，质量大于数量底线不能破，带看质量不行直接换备选。销售B汇报老带新进展：奖励政策为成功一套奖励两万现金或等值车位券，本月推四组、两组在谈，老业主需话术和礼品支持。组长准备定制伴手礼，包括高端茶叶礼盒和定制保温杯。
+## 00:08:43-00:10:08 老业主痛点与目标分解
+销冠指出老业主怕麻烦，建议搞“业主推荐官”活动，每成功推荐一套不仅给钱，还可升级物业服务等级，如优先预约维修、免费家政清洗一次，软性权益更易在小区群传播。总监认可软硬结合，要求组长下周前出详细执行表。随后总监宣布下月集团指标为总去化一百二十套，比上月多百分之五十。组长按人员配置和上月产出权重拆分：销冠目标二十八套，组长、销售A、销售B三人一组目标五十套，剩余十二套作为机动和渠道攻坚储备。总监确认拆分合理，但强调压力在销售A和销售B身上。
+## 00:10:19-00:12:10 表态与周末答谢会安排
+销售A表态能扛，手头有十五个准客户在等下周认筹通知，只要逼定话术统一、配合组长资源倾斜，五十套盘子三人能完成，但希望渠道带看质量再筛一筛。销售B计划周末搞小型业主答谢会，邀请已成交业主分享并推老带新政策，氛围好能提升转化率。销冠表示支持，可带人协助盯两桌，其改善型客户与答谢会客群重合度高，可做联动把高意向客户拢到一起周末集中去化。总监安排分工：销冠带人协助，销售B主抓流程，销售A负责客户邀约和逼定记录。同时宣布本周安排两次专项培训，分别为“竞品对比与抗性化解”和“逼定时机与谈判心理学”，每人必须参加，课后现场抽考，不过加练，组长盯进度并安排签到和考核表，结果挂钩下周绩效系数。
+## 00:12:29-00:15:07 销控纪律与会议总结
+组长提出销控表更新延迟，客户定后销售仍推同套房源易引起客诉。总监强调这是底线问题，要求销控实时同步，谁推哪套必须在群里喊一声、CRM系统同步锁房，下月再出现销控不同步丢单或客诉直接问责，组长定纪律并设专人每小时刷新销控大屏。组长总结五项核心议题：工地开放日周三固定开放、逼定权益可视化替换旧物料、渠道带看实名制与质量考核、周末业主答谢会联动去化、专项培训与销控纪律。销售A建议邀约话术统一为“老业主专属品鉴宴”，避开“促销”字眼，销售B随即修改邀约短信和电话模板。销冠补充逼定时财务和法务最好在洽谈区待命，现场能签当场出数出收据，客户安全感强，成交率能提至少两成。总监协调财务和法务周六日轮流值班在案场外围，要求组长散会后半小时内把会议纪要和任务分解表发到工作群，销冠下周晨会分享逼定案例，销售A、销售B盯紧周末答谢会，总监负责渠道和工程对接。
+# 要点梳理
+## 上月销售数据复盘
+- **总到访**：上月案场总到访320组，环比增加15%，数据达标。
+- **成交与转化**：成交76套，转化率23%，较上月27%下降4个百分点。
+- **来访结构**：渠道带看占比65%，自然来访仅35%。
+- **蓄客与流失**：蓄客量约3200组，认购到成交流失率约18%。
+- **流失抗性**：客户流失集中在两个抗性——价格预期（竞品推特价房、首付分期、送物业费等）与交付信心（客户细问园林选材、车库层高、外墙保温层）。
+- **结论**：量够但转化不足，卡在逼定和转化环节，自主拓客能力和案场拦截能力退化。
+## 工地开放日标准化
+- **问题**：工地开放日频率不足，客户自行看房不便，陪看占用销售时间；报备审批流程繁琐，需半天。
+- **决定**：工地开放日定为每周三下午固定开放，提前两天在CRM系统推送意向客户，客户直接对接专属顾问，不走复杂流程。
+- **依据**：销售A分享改善型客户案例，三次带看均请施工经理现场答疑，客户因工程透明最终成交。
+## 逼定策略与权益可视化
+- **销冠方法**：不直接降价，采用“算总账”方式——将物业费、车位管理费、装修损耗拉表对比竞品，说明单价虽高2000元但十年省下物业和品质维修维护费；配合“限时权益”逼定函，承诺本周定下可申请多送三年物业费。
+- **销售B补充**：客户对“限时权益”不买账，需将权益具象化——把三年缴费明细打印放在合同旁。
+- **物料问题**：现场逼定函常为上月版本，组长已记录，联系设计本周出新版，写清权益条款避免歧义；下月制作“权益可视化”台卡放洽谈区。
+## 渠道带看质量管控
+- **问题**：渠道带看量上升但无效带看多，多为中介随便凑数。
+- **决定**：下月起带看必须实名登记，需明确需求标签，否则扣减渠道积分；质量不行直接换备选。
+- **风险**：销售A反馈中介抵触，称其他楼盘不查此要求，怕渠道不愿推盘；总监表示亲自与渠道部沟通，质量大于数量底线不破。
+## 老带新政策与业主答谢会
+- **奖励政策**：老带新成功一套奖励两万现金或等值车位券。
+- **当前进展**：销售B本月推四组，两组在谈，客户反馈老业主有面子、奖励实在；老业主不好意思开口，需提前给话术和礼品支持。
+- **伴手礼**：组长准备定制高端茶叶礼盒和保温杯，老业主转介绍时直接送。
+- **业主推荐官活动**：销冠建议每成功推荐一套，除现金外升级物业服务等级（优先预约维修、免费家政清洗一次），软性权益更易在小区群传播。
+## 下月目标分解与专项培训
+- **总目标**：集团指标下月总去化120套，比上月多50%。
+- **拆分**：销冠28套；组长、销售A、销售B三人一组共50套；剩余12套作为机动和渠道攻坚储备。
+- **表态**：销售A手头15个准客户等下周认筹通知，需逼定话术统一和组长资源倾斜；销售B计划周末办小型业主答谢会，邀请成交业主分享并推老带新政策。
+- **培训安排**：本周两次专项演练——“竞品对比与抗性化解”“逼定时机与谈判心理学”，每人必须参加，课后现场抽考，不过加练；组长安排签到和考核表，结果挂钩下周绩效系数。
+## 销控纪律与流程优化
+- **问题**：销控表更新延迟，客户定后销售仍推同套房源，易引起客诉。
+- **决定**：销控必须实时同步，谁推哪套在群里喊一声，CRM系统同步锁房；下月再出现销控不同步丢单或客诉直接问责。
+- **执行**：组长在晨会上强调，设置专人每小时刷新销控大屏。
+## 会议总结与后续安排
+- **邀约话术**：销售A建议统一为“老业主专属品鉴宴”，避开“促销”字眼，客户抵触心理小；销售B即改邀约短信和电话模板。
+- **财务法务待命**：销冠建议逼定时财务和法务在洽谈区待命，现场能签当场出数出收据，成交率可提升至少两成；总监协调周六日轮流值班在案场外围。
+- **会后任务**：组长散会后半小时内发会议纪要和任务分解表到工作群；销冠下周晨会分享逼定案例。
+## 结论与决定
+- 工地开放日定为每周三下午固定开放，提前两天在CRM系统推送意向客户。
+- 逼定权益可视化，本周内更新逼定函物料，下月制作权益可视化台卡。
+- 渠道带看必须实名登记并明确需求标签，否则扣减渠道积分。
+- 下月总去化目标120套：销冠28套，组长、销售A、销售B三人组50套，剩余12套机动。
+- 周末举办业主答谢会，销售B主抓流程，销售A负责邀约和逼定记录，销冠带人协助。
+- 销控必须实时同步，CRM系统同步锁房，下月再出现销控不同步丢单或客诉直接问责。
+- 财务和法务周六日轮流值班在案场外围。
+## 行动项与分工
+- **组长**：制定工地开放日标准化方案（每周三固定开放、提前两天CRM推送）；联系设计本周出新版逼定函；准备定制伴手礼；设置专人每小时刷新销控大屏；散会后半小时内发会议纪要和任务分解表到工作群。
+- **销冠**：梳理手头二十几个高意向客户，周末配合答谢会带人协助；下周晨会分享逼定案例。
+- **销售A**：周末答谢会负责客户邀约和逼定记录；配合组长回访上周未成交客户；统一邀约话术为“老业主专属品鉴宴”。
+- **销售B**：周末答谢会主抓流程；修改邀约短信和电话模板；推进老带新业务。
+- **总监**：与渠道部沟通实名制要求；协调财务和法务周六日值班。
+## 待确认与风险
+- 渠道带看质量差、无效带看多，可能影响转化。
+- 中介对实名制有抵触，可能影响渠道推盘意愿。
+- 现场物料更新慢，逼定函版本滞后可能影响逼定效果。
+- 销控表更新延迟可能引起客诉。</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4211/4712</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="13.5" customHeight="1" s="9">
       <c r="A56" s="7" t="inlineStr">
@@ -16140,6 +17672,80 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次团队例会由组长主持，A与B两位成员参与，主要同步ASR模型迭代进度，并解决线上推理延迟与长音频卡死问题。会议围绕数据清洗与模型训练、推理延迟优化、长音频卡死修复、监控与自动化评估体系建设、前端采样率升级五个板块展开。关键结论为：确认流式RNN-T混合架构与2秒切分方案，稳定性优先、精度次之，下周先出热修复版本上灰度。关键数字锚点：有效语音时长占比从89%提升至94%，验证集WER下降0.8个百分点，首字延迟目标控制在80ms以内，热修复版本周四提测。
+# 分段速览
+## 00:00:00-00:00:58 开场与数据训练进展
+组长开场明确会议目标：过一遍上周ASR模型迭代进度、线上推理延迟和长音频卡死问题，要求A和B分别同步各自板块现状并直接提出卡点或资源需求。A汇报数据清洗流水线已完成第二轮，将长尾噪音、极端口音和背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%左右；同时重新校对CTC的blank token分布，发现多音字和连读场景切分点存在偏移，计划用新基准跑一轮消融。B反馈验证集WER下降约0.8个百分点，但指出低资源语言混合边界场景下切分仍有毛刺，中英文切换时模型容易吞掉过渡音或重复解码。
+## 00:00:58-00:02:55 架构调整与显存评估
+A回应边界切分问题源于CTC对齐阶段对跨语言边界和轻声尾音处理不够平滑，计划将全纯Transformer架构换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练；数据增强策略已加入时间偏移，但对背景白噪声和混响鲁棒性不足，准备引入MixUp和CutMix再迭代。B认可混合架构方向，但提出RNN-T缓存机制和显存占用问题——GPU集群虽为A100，并发量上升时KV Cache显存峰值容易飙高，可能导致线上服务OOM。A回应已评估该问题，计划对RNN-T的prefix LM缓存做INT8量化并配合动态缓存释放策略，预计压降30%左右显存占用，但压测数据尚未跑完，明天下午将日志和截图发群里同步阈值。
+## 00:02:55-00:04:35 推理延迟优化方案
+B汇报推理侧卡点集中在动态Batching调度逻辑：线上请求长短音频混排，现有队列切分导致首字延迟波动在150ms到300ms之间，产品反馈体验不连贯。计划将动态Batching改为静态分段加流式解码组合方案——音频按2秒切块，前端VAD预过滤，后端用RNN-T增量解码，目标首字延迟控制在80ms以内，整体吞吐量稳定在120路并发。VAD阈值暂定-25dB，结合能量和谱熵双模型判断，但真实线上底噪更复杂，下周将拉线上流量回放做端到端对比。A提醒VAD阈值需平衡误切率和漏切率，阈值过高会切掉轻声尾音导致缺字，过低则产生多余切分增加无效推理，并要求拉回放时打点前后帧特征日志以便排查切分点对齐影响。
+## 00:04:35-00:06:43 组长指导意见与自动化评估
+组长确认调整方向并提出三点要求：流式架构切换不能影响现有非流式离线批处理，双线都要保且测试用例覆盖全；VAD阈值由B做消融实验，画误切率和漏切率曲线找最优解；A的模型训练算力已协调，下周一开始划拨三块A100做增量训练，需注意与NLP组错峰使用。A回应将离线和流式验证集分开跑，测试用例周五前发评审，并调整启动脚本优先跑验证集小的实验、大训练放周末夜间；同时提出用GitLab CI搭建自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码、结果对比，WER未下降或RTF超标直接打回。组长认可并要求B将压测脚本也挂上去形成闭环，A预计三天完成，周四前出V1版本，B配合将压测数据输出为标准JSON格式。
+## 00:06:43-00:08:49 长音频卡死问题与热修复
+B报告线上特殊场景报错：用户输入超长连续且带方言口音的音频时，解码器陷入无效循环导致loop卡死，直接触发服务器节点重启。当前解码器默认max steps为2048个token、超时5秒，但部分音频解码序列长度超阈值后解码器未做优雅降级直接OOM，日志显示RNN-T的attention权重一直震荡未收敛。A建议增加early stopping机制，结合置信度阈值和连续低概率token判断——连续30步置信度低于0.2时强制截断并返回当前序列，预计能解决90%以上卡死问题。B将实现该逻辑并配合超时熔断和降级返回，同时询问输出序列长度受限是否影响专业术语或长句完整识别。组长明确稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度，B今晚改完周四提测，A配合长序列数据配比和边界用例验证。
+## 00:08:49-00:10:56 监控体系与采样率升级
+B提出日志系统过于简陋，线上推理的中间特征和中间帧无法落盘，排查问题全靠猜测，计划接入Prometheus和Grafana监控面板，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标。组长认可需求并协助对接运维，要求明天下班前出监控指标定义文档，告警阈值分P0和P1两级——P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增。随后B指出前端SDK音频采样率仍为16k而新模型为32k输入，前端不升级则上采样会引入高频伪影影响识别率，前端对接人称排期推至下月。组长表示32k模型在长尾词上WER比16k好0.5%，将拉产品和技术总监优先插队推进；备选方案为服务端加实时重采样模块做兼容但会增加CPU开销。A建议先由B写轻量级重采样插件用libresample实测CPU占用和延迟影响再决策，B同意先出压测对比数据，CPU开销控制在5%以内再提方案。
+## 00:10:56-00:11:57 总结与收尾
+组长总结今日要点：第一，流式RNN-T混合架构和2秒切分方案由A和B分头推进，本周五前出详细设计和压测数据；第二，VAD阈值和长序列解码卡死问题，B周四出消融报告和热修复方案，A配合长序列数据配比和评估流水线对接；第三，前端32k采样率升级，B出对比文档和重采样插件实测，组长拉会推进；第四，监控面板和CI自动评估流水线本周内定稿并开始对接运维和测试环境。A确认周三前将CI脚本和测试用例发群里评审，B确认负责推理优化、VAD消融、热修复和监控文档，会议结束。
+# 要点梳理
+## 数据清洗与模型训练
+- **数据清洗**：混合语料库清洗流水线完成第二轮，长尾噪音、极端口音、背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%
+- **WER表现**：验证集WER下降0.8个百分点；低资源语言混合边界场景下，中英文切换时模型易吞音或重复解码
+- **架构调整**：计划将全纯Transformer架构更换为流式RNN-T与Transformer混合形态，先在20小时核心数据上训练
+- **数据增强**：已加入时间偏移，对背景白噪声和混响鲁棒性不足，准备引入MixUp和CutMix再迭代一轮
+- **CTC对齐**：重新校对blank token分布，发现多音字和连读场景切分点有偏移，本周用新基准跑消融
+## 推理延迟优化
+- **现状问题**：动态Batching在长短音频混排时首字延迟波动在150ms到300ms之间，产品反馈体验不连贯
+- **调整方案**：改为静态分段加流式解码组合方案——音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码
+- **性能目标**：首字延迟控制在80ms以内，整体吞吐量稳定在120路并发
+- **VAD阈值**：暂定-25dB，结合能量和谱熵双模型判断；需平衡误切率和漏切率，阈值过高切掉轻声尾音致缺字，过低增加无效推理
+- **验证计划**：下周拉线上流量回放做端到端对比，前后帧特征打点日志便于排查切分点对齐影响
+- **显存评估**：RNN-T的prefix LM缓存拟做INT8量化配合动态缓存释放策略，预计压降30%左右显存占用；压测日志和截图明天下午发群同步阈值
+## 长音频卡死问题
+- **故障现象**：线上超长连续带方言口音音频导致解码器loop卡死，陷入无效循环，直接触发服务器节点重启
+- **参数现状**：解码器默认max steps为2048个token，超时时间5秒；部分音频解码序列超阈值，解码器未做优雅降级直接报OOM
+- **根因分析**：RNN-T的attention权重持续震荡未收敛
+- **修复方案**：增加early stopping机制——连续30步置信度低于0.2时强制截断并返回当前序列，预计解决90%以上卡死问题；同时实现超时熔断和降级返回
+- **处理原则**：组长明确稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度
+## 监控与自动化评估
+- **监控面板**：接入Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标
+- **告警分级**：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增；监控指标定义文档明天下班前发组长，由组长转发运维负责人
+- **CI评估流水线**：用GitLab CI实现代码合入即触发数据拉取、模型加载、测试集解码、结果对比；WER未下降或RTF超标直接打回
+- **落地时限**：A负责评估脚本和流水线配置，预计三天，周四前出V1版本；B配合将压测数据输出为标准JSON格式
+## 前端采样率升级
+- **问题**：前端SDK音频采样率16k，新模型输入32k，上采样引入高频伪影影响识别率；32k模型在长尾词上WER比16k好0.5%
+- **排期冲突**：前端对接人称排期推至下个月
+- **推进方案**：B出对比文档和重采样插件实测（用libresample，CPU开销控制在5%以内），组长拉产品和技术总监优先插队；备选方案为服务端加实时重采样模块，但会增加CPU开销和推理链路延迟
+## 结论与决定
+- **稳定性优先，精度次之**：长音频卡死问题先出热修复版本上灰度，专业术语识别后续通过词表扩展和热词注入解决
+- **架构方向确认**：流式RNN-T混合架构和2秒切分方案方向可行，但流式架构切换不能影响现有非流式离线批处理，双线都要保，测试用例需全覆盖
+- **算力协调**：组长协调下周一划拨三块A100做增量训练，需与NLP组错峰使用，注意调度面板排队
+## 行动项与分工
+- **A**：本周五前出流式RNN-T混合架构详细设计和压测数据；周三前把CI脚本和测试用例发群评审；周四前出评估流水线V1版本；配合长序列数据配比和边界用例验证
+- **B**：今晚改完热修复版本，周四提测；周四出VAD阈值消融报告和热修复方案；明天下班前发监控指标定义文档；出前端32k对比文档和重采样插件实测
+- **组长**：明天拉产品和技术总监过前端32k采样率升级事项；将监控指标文档转发运维负责人
+- **算力调度**：A调整启动脚本，优先跑验证集小的实验，大训练放周末夜间，避开NLP组四个排队job
+## 待确认与风险
+- **显存压测未完成**：RNN-T的prefix LM缓存INT8量化配合动态缓存释放策略的具体显存曲线和压测数据未跑完，明天下午发群同步阈值
+- **VAD阈值待验证**：-25dB阈值在真实线上底噪环境下是否最优，需通过线上流量回放验证误切率与漏切率平衡
+- **热词注入影响待确认**：流式解码和静态切分的衔接是否影响热词注入的实时生效，待技术细节验证
+- **服务端重采样待决策**：是否采用服务端实时重采样模块需B先出压测对比数据（CPU开销控制在5%以内）再决策
+- **OOM风险**：并发量上升时KV Cache显存峰值易飙高，可能导致服务OOM
+- **算力冲突**：与NLP组项目存在GPU排队撞车风险，需错峰运行</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3912/4913</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/now.xlsx
+++ b/now.xlsx
@@ -567,66 +567,56 @@
       <c r="C2" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲，阐述中国对多极化世界的立场。演讲围绕推动平等有序的世界多极化这一主题，提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，中国将坚定做多极体系中的确定性因素，做变革世界中的建设性力量。在随后的问答环节，王毅就国际秩序与规则、乌克兰危机、中美关系等议题回应了主持人提问。
+王毅在慕尼黑安全会议上发表演讲并回答提问，围绕推动平等有序的世界多极化这一主题，提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，中国将坚定做变革世界中的建设性力量，是多极体系中的确定性因素。演讲援引慕安会报告主题指出世界走向多极化，并提及联合国会员国从80年前的51个增至193个、中国承担超过20%的联合国会费、去年中国GDP增长5%等关键数字。问答环节涉及国际秩序与规则、乌克兰危机、中美关系等议题；会后王毅将前往纽约出席联合国安理会会议。
 # 核心信息
-## 多极化主张
-- **总体立场**：中国主张推动**平等有序的世界多极化**，这是习近平主席提出的重大主张；中国将坚定做多极体系中的确定性因素、变革世界中的建设性力量。
-- **平等相待**：坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
-- **国际法治**：联合国宪章宗旨和原则是国际关系根本遵循；中国加入几乎所有普遍性政府间国际组织和**600多项国际公约**，从不搞例外主义、不搞合则用不合则弃。
-- **多边主义**：坚持真正的多边主义，倡导共商共建共享的全球治理观；坚定维护联合国权威和地位，承担**超过20%的联合国会费**。
-- **开放共赢**：坚持开放合作，以普惠包容的经济全球化支撑平等有序的世界多极化；去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**。
-## 具体行动与倡议
-- **全球治理公共产品**：提出并落实全球发展倡议、全球安全倡议、全球文明倡议；切实履行巴黎协定，建成世界上最大的清洁发电体系。
-- **共建一带一路**：愿推动高质量共建“一带一路”，与欧盟“全球门户”战略相互对接。
-- **中欧关系**：中方始终认为欧洲是多极世界的重要一极，中欧是伙伴而不是对手；今年是中欧建交50周年，愿用好这一契机深化战略沟通和互利合作。
-## 国际秩序与规则
-- **秩序立场**：中国是在现行国际秩序中发展起来的受益者，要推动秩序朝着更加公正合理的方向发展；真正挑战秩序、毁约退群的是其他国家。
-- **规则共识**：应共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则；反对在遵守国际法上搞双重标准。
-- **台湾问题**：要尊重各国主权和领土完整，就应该支持中国实现完全统一。
+## 多极化主张与总体判断
+- **时代判断**：当前世界更加变乱交织，借用2025年慕安会报告主题，世界正走向多极化；80年前联合国成立时仅51个会员国，如今已有193个国家。
+- **中国主张**：推动平等有序的世界多极化，系习近平主席提出的重大主张；中国将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。
+- **四点看法**：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢，作为建设多极世界的基本原则。
+## 平等相待与国际法治
+- **平等原则**：坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；慕安会近年邀请更多全球南方国家出席会议系明智之举。
+- **国际法治**：联合国宪章宗旨和原则是国际关系根本遵循；国家不论大小强弱都是国际法治的利益攸关方，大国应带头讲诚信、讲法治，摒弃言行不一和零和博弈。
+- **中国实践**：加入几乎所有普遍性政府间国际组织和**600多项国际公约**，从不搞例外主义，不搞合则用、不合则弃；在遵守国际法上不能搞双重标准，尊重各国主权和领土完整就应支持中国实现完全统一。
+## 多边主义与开放共赢
+- **多边主义**：联合国是践行多边主义、推进全球治理的核心平台，已为各国遮风挡雨80年；应固本强基而非拆梁毁柱，对全球难题共担责任而非唯利是图，团结应对而非阵营对抗。
+- **中国贡献**：坚定维护联合国权威和地位，承担**超过20%的联合国会费**；切实履行巴黎协定，建成世界上最大的清洁发电体系；提出并落实全球发展倡议、全球安全倡议、全球文明倡议。
+- **开放共赢**：保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己；应以普惠包容的经济全球化支撑平等有序的世界多极化。
+- **经济数据**：2024年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**；中国愿推动高质量共建“一带一路”，与欧盟“全球门户”战略相互对接。
+- **中欧关系**：欧洲是多极世界重要一极，中欧是伙伴而非对手；2025年系中欧建交50周年，中方愿深化战略沟通和互利合作。
 # 官方表态
-**官方表态**（中国，王毅，慕尼黑安全会议）
-## 多极化主张
-- **主张**：应当推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是中国对多极世界真诚的期许；中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。
-- **针对**：多极化是否会带来动荡失序、冲突对抗是否意味着大国主导弱肉强食的疑问。
-- **承诺**：中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；这不会导致西方的缺失，而将促进世界的正和。
-- **边界**：中国从不搞例外主义，更不搞合则用、不合则弃。
-## 国际法治
-- **主张**：应当尊重国际法治，联合国宪章宗旨和原则是处理国际关系的根本遵循，也是建设多极世界的重要基石；多极格局不能是无序的状态。
-- **针对**：当今世界乱象频出，有些国家迷信实力至上，打开了丛林法则的潘多拉盒子。
-- **要求**：大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈；在遵守国际法上不能搞双重标准。
-- **承诺**：中国坚定维护国际法治权威，积极履行国际责任和义务，加入了几乎所有普遍性的政府间国际组织和600多项国际公约。
-- **条件**：要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
-## 多边主义
-- **主张**：应当践行多边主义，联合国是践行多边主义、推进全球治理的核心平台；对于这座大厦应该固本强基，而不是拆梁毁柱。
-- **针对**：面对层出不穷的全球性挑战，搞本国优先只会造成各方的多输。
-- **承诺**：中国坚持真正的多边主义，倡导共商共建共享的全球治理观，坚定维护联合国的权威和地位，承担着超过20%的联合国会费；切实履行巴黎协定，建成了世界上最大的清洁发电体系；提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
-## 开放共赢
-- **主张**：应当坚持开放合作，以普惠包容的经济全球化来支撑平等有序的世界多极化；保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己。
-- **承诺**：中国坚定同各国共享发展机遇，愿推动高质量共建"一带一路"，同欧盟"全球门户"战略相互对接，赋能彼此也赋能世界。
-- **针对**：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。
-- **定位**：中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手；今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作。
-## 国际秩序与规则
-- **主张**：中国是在现行国际秩序中发展起来的，是受益者；要推动这个秩序朝着更加公正合理的方向发展。
-- **针对**：有人说中国要改变秩序、要另起炉灶；真正要挑战秩序、毁约退群的国家已经出现。
-- **要求**：需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数；只要认同这一点，双重标准就不会出现。
-## 人类命运共同体
-- **主张**：习近平主席提出各国共同构建人类命运共同体的重大理念，希望各国超越历史文化社会制度意识形态的不同，以同舟共济的精神共同呵护人类唯一可以居住的星球。
-- **承诺**：中国将继续为践行这些重要理念做出努力和贡献；这体现了中国共产党的国际主义情怀和天下为公的中华优秀文化传统。
+## 关于多极化世界
+- **主张**：中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是中国对多极世界真诚的期许；中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。
+- **平等相待**：坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权，这不会导致西方的缺失，而将促进世界的正和。
+- **尊重国际法治**：联合国宪章宗旨和原则是处理国际关系的根本遵循，也是建设多极世界的重要基石；多极格局不能是无序状态，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈。
+- **践行多边主义**：联合国是践行多边主义、推进全球治理的核心平台，对这座大厦应该固本强基，而不是拆梁毁柱；中国坚持真正的多边主义，倡导共商共建共享的全球治理观。
+- **开放共赢**：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界；保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己；应当坚持开放合作，以普惠包容的经济全球化来支撑平等有序的世界多极化。
+## 关于国际秩序与规则
+- **主张**：中国是在现行国际秩序中发展起来的，是这一秩序的受益者；要做的不是另起炉灶，而是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向发展。
+- **共同认知**：需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数；只要认同这一点，双重标准就不会有存在的空间。
+- **承诺与边界**：中国坚定维护国际法治权威，积极履行国际责任和义务，从不搞例外主义，更不搞合则用、不合则弃；在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
+## 关于乌克兰危机
+- **中俄关系**：中国同俄罗斯建立了不结盟、不对抗、不针对第三方的睦邻友好关系，两国交往是正常的国与国之间的交往；中国从俄罗斯进口油气是出于满足民众需求的现实考量，不会允许国家把经贸问题政治化、当作打压中国的工具。
+- **中方立场**：一切争端和冲突都应该通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题；自2022年2月25日起中方即提出对话协商解决，习近平主席提出4点主张——各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。
+- **劝和促谈**：中国以此为依据不断推进劝和促谈，派特使赴各国斡旋，同巴西等南方国家发起"和平之友"；中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应适时参与和谈进程，欧洲更有必要为此发挥重要作用。
+## 关于中美关系
+- **政策连续性**：中国对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现了作为大国的战略定力和国际信誉；对美政策就是习近平主席提出的三原则——相互尊重、和平共处、合作共赢。
+- **前提与条件**：中美制度不同是各自人民做出的选择，想改造或颠覆对方是不切实际的，相互尊重是中美交往的前提；中方愿意按照三原则同美方构建稳定健康可持续的双边关系，希望美方相向而行。
+- **承诺与边界**：如果美方仍然对中国打压和遏制，中方别无选择，必将奉陪到底，坚定维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边和霸凌行径；中国这样做也是为了维护国际公平正义和国际关系基本准则。
 # Q&amp;A环节
-**1. 主持人**：您提到国际秩序，现在很多国家质疑联合国宪章。俄罗斯入侵乌克兰，美国总统威胁使用武力入侵格陵兰和巴拿马、驱逐巴勒斯坦人，中国也被指责违反海洋法和《世界人权宣言》。您即将前往纽约参加安理会会议，您还相信联合国和联合国宪章吗？是否致力于推动联合国改革？
-**王毅**：我不愿意回答周琦先生的提问。关于秩序，这几年总有人说中国要改变秩序、另起炉灶，但现在说这种话的人可能不多了，因为真正挑战秩序、毁约退群的国家出现了。中国是在现行国际秩序中发展起来的，是受益者，我们要做的是按照大多数国家的愿望推动秩序朝更加公正合理的方向发展。关于规则，我们起码应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。只要大家认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字、治理赤字，共同构建人类命运共同体。
-**2. 主持人**：2022年慕安会前几天您曾说任何国家的主权、独立和领土完整都应得到尊重和维护，乌克兰也不例外。如今俄罗斯已成为中国有军队的加油站，您对乌克兰有很大影响力。现在压力加大，您能否采取措施，比如减少从俄罗斯购买天然气、降低价格或停止输送军民两用物资，以施压俄罗斯结束战争？
-**王毅**：中国同俄罗斯是两大邻国，有着漫长边界，两国关系经历过曲折后吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。如果中国不从俄罗斯买油气，哪个国家能提供如此巨量的油气满足中国民众需求？那是不可能的，也是不保险的，因为有的国家常把经贸问题政治化，当作打压中国的工具。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。我们派特使斡旋，同巴西等南方国家发起和平之友。中方乐见一切和平努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应适时参与和谈进程。这场战事发生在欧洲大地上，欧洲更有必要发挥重要作用，共同探讨欧洲长治久安，找到均衡有效可持续的欧洲安全框架。
-**3. 主持人**：时间有限，能否简要预告您认为美中关系将如何发展？
-**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不一样，是各自人民做出的选择，想改造或颠覆对方不切实际。相互尊重是中美交往的前提，和平共处理所当然，中美两个大国总不能冲突起来，那将殃及整个世界。中方已准备好按照三原则同美方构建稳定健康可持续的双边关系。我们希望美方相向而行，但如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼，对世界前途和中美关系的未来都充满信心。中美两国只有一个共同努力的方向，就是相互尊重、和平共处、合作共赢。</t>
+**1. 主持人**：您提到国际秩序，我注意到各方对联合国宪章提出质疑——俄罗斯入侵乌克兰、美国总统威胁对格陵兰和巴拿马动武、巴勒斯坦人流离失所，贵国也被指违反海洋法和《世界人权宣言》。您即将前往纽约出席安理会会议，您是否仍相信联合国和联合国宪章？宪章改革在您的议程中优先级有多高？
+**王毅**：你提问涉及秩序和规则两个关键词。关于秩序，这几年有人说中国要改变秩序、另起炉灶，但现在说这种话的人不多了——真正挑战秩序、毁约退群的国家出现了，欧洲朋友可能每天都在感受阵阵寒意。中国是在现行国际秩序中发展起来的，是受益者，我们要做的是按大多数国家愿望推动秩序朝更加公正合理的方向发展。关于规则，我们起码应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。只要认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字、治理赤字，共同构建人类命运共同体。
+**2. 主持人**：2022年慕安会前几天您曾表示任何国家的主权、独立和领土完整都应得到尊重，乌克兰也不例外。如今俄罗斯已成为中国有军队的加油站，您对乌克兰有很大影响力。在各方加大施压结束战争之际，您能否采取措施——比如减少从俄罗斯购气、降低价格或停止输送两用物资——以加大对俄压力？
+**王毅**：中国同俄罗斯是两大邻国，有着漫长边界。两国关系曾经历曲折，之后双方吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。关于是否不从俄罗斯买油气——如果中国不从俄罗斯买，哪个国家能提供如此巨量油气满足中国民众需求？那不可能，也不保险，因为有的国家常把经贸问题政治化、当作打压中国的工具，我们不会允许这种情况，要为人民负责。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。我们派特使斡旋，同巴西等南方国家发起"和平之友"。任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括美俄达成的共识；所有当事方和利益攸关方都应适时参与和谈，欧洲更有必要为此发挥重要作用。
+**3. 主持人**：时间所限，能否简要预告您对中美关系将如何发展的看法？
+**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度确实不一样，这是各自人民的选择，想改造或颠覆对方不切实际。相互尊重是中美交往的前提，和平共处理所当然——两个大国总不能冲突起来，那将殃及整个世界。中方已准备好按三原则同美方构建稳定健康可持续的双边关系，希望美方相向而行；如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼。我们对世界前途和中美关系的未来都充满信心，中美共同努力的方向就是相互尊重、和平共处、合作共赢。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>45.3</v>
+        <v>42.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/3762</t>
+          <t>7004/4045</t>
         </is>
       </c>
     </row>
@@ -793,80 +783,84 @@
       <c r="C3" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-本次宣讲会由电子科技大学电子科学与工程学院主办，面向考生和家长介绍学院整体情况、学科方向、师资科研与人才培养，并解答夏令营等问题。学院源于1956年建校时的无线电系，历经4次院系调整，2023年成立电子科学与工程学院与基层电路学院；电子科学与技术为国家重点一级学科，下设5个二级学科方向，另有3个国防特色学科。本科生1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业）和电磁场与无线技术（国家级一流本科专业建设点）；研究生1975人。现有教师302人，其中两院院士2人、领军人才19人、青年人才28人；近5年科研经费到账稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利授权1300余件。电子信息材料与元器件方向由柳教授介绍，以材料为基础、器件为核心、应用为目标导向，涉及电子材料与电子器件的设计、研制、生产与应用。2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍，先进电子材料元器件电路系统等为卡脖子问题之一。研究团队包括邓龙江院士的电磁辐射控制材料与技术团队（19人，正高13人、副高15人）和张怀武教授的磁电薄膜与微型器件团队（17人，正高15人、副高2人），依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室两个国家级平台。科研面积2万余平米，大型设备500余台套；获国家科技奖项共7项，毕业生去向包括英特尔、中芯国际、华为、德州仪器等。电磁场与微波技术、电路与系统方向由张教授介绍。电磁场与微波技术包含4个细分方向，电路与系统包含3个方向；电磁场与微波技术学科始于1956年，由林卫干先生和谢楚芳先生创建，所属一级学科入选双一流A类。硬件平台拥有中国高校最先进的微波暗室群体和微波毫米波太Hz仿真测试平台。杨世文教授团队的四维天线阵列技术应用于中电14所某大型机载相控阵雷达；樊勇教授团队研制出0.22THz、0.34THz、0.42THz雷达成像系统，分辨率小于1厘米，成果在2023年成都大运会田径项目示范应用。电路与系统学科1981年开始招收研究生，1988年成立首批博士后流动站，拥有国家级人才4人、教授10人、副教授22人。物理电子学方向由李天明教授介绍，是物理学与电子科学与技术的交叉学科，典型应用包括微波电子学、光电子学等。学校物理电子学起源于1956年建校时的电子控器件专业，1979年成立高能电子学研究所，2018年并入电子科学与工程学院。纵向发展包括上游仿真设计（如自主知识产权商用软件MMST和切皮克）和下游系统应用（如毫米波雷达、无线输能系统、微波能干燥系统）；横向发展包括频段上移至毫米波、太赫兹，以及与医学交叉的太赫兹成像诊断。每年到校科研经费接近2亿元，为学院最多；团队学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他。学生代表田雨桐（2023级电子科学与技术专业博士研究生）从学生视角分享选择电子学院的8个理由，包括城市（成都为四川省会、国家中心城市、新一线城市，电子信息产业发达）、学校（电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一）、专业、团队（学院拥有四大学科和19个科研团队）、奖助体系等。田雨桐所在毫米波技术与系统应用团队负责人为樊勇老师，研究方向覆盖微波毫米波理论与技术、天线理论与技术等五大方向；团队硕博毕业生就业率100%，就业单位包括民营企业、大型央国企和头部科研院所。建议先选研究团队再选导师，可通过学院网站、文献检索网站（如IEEE、中国知网）了解导师情况。互动环节中，主持人询问夏令营时间形式，段院回应电子学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群发布；咨询QQ群号确定为978499108。抽奖口令为“E生一世，逐梦未来”。
+本次直播由电子科技大学电子科学与工程学院面向考生和家长举办，旨在介绍学院整体情况与各学科方向，吸引优秀生源报考。学院段院、柳教授、张教授、李天明教授及博士生田雨桐分别就学院历史沿革与学科设置、电子信息材料与元器件、电磁场与微波技术、电路与系统、物理电子学等方向进行宣讲，并从学生视角分享择校与专业选择建议。整体基调为积极推介，直播中主持人还就考生关心的夏令营安排进行提问，段院回应学院计划今年举办夏令营但时间待定，相关信息将通过QQ群发布。
 # 核心信息与数据
 ## 学院概况
-- **历史沿革**：1956年建校时成立无线电系、电真空器件系、无线电零件系，历经1979年、1992年、2001年、2018年4次院系调整成立电子科学与工程学院（示范性微电子学院），2023年响应国家号召成立电子科学与工程学院与集成电路学院。
-- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向；另有电磁场与微波军用关键材料、电子元器件等3个国防特色学科。
+- **历史沿革**：1956年建校之初成立无线电系、电真空器件系、无线电零件系，历经1979年、1992年、2001年、2018年4次院系调整成立电子科学与工程学院（示范性微电子学院），2023年响应国家号召成立电子科学与工程学院与集成电路学院。
+- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有电磁场与微波、军用关键材料、电子元器件3个国防特色学科。
 - **党建荣誉**：学院党委入选教育部首批全国党建工作标杆院系，学院荣获全国教育系统先进集体。
-- **人才培养规模**：本科生现有1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业）和电磁场与无线技术（国家级一流本科专业建设点）两个专业方向；研究生现有硕士和博士1975人，招生专业包括电子科学与技术、材料科学与工程等。
-- **师资队伍**：现有教师302人，其中教研系139人、科研系95人、教学系14人、实验系21人、机关33人；两院院士2人、领军人才19人、青年人才28人、其他类型人才12人。
-- **科研经费与成果**：近5年科研经费到账稳定在3—4亿元之间，项目以纵向为主、横向为辅；牵头获国家科技奖励11项，发表高水平学术论文2000余篇，专利申请1600余件、授权1300余件。
-- **科研团队与平台**：共有20个科研团队，年度经费过千万元的团队15个、过亿元团队1个；拥有国家电磁辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室两个国家级平台，4个国际合作平台、7个省部级科研平台。
-- **国际交流**：共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
+- **人才培养规模**：本科生现有1545人，招生专业为工科试验班（电子工程类），含电子科学与技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向；硕士和博士研究生1975人，学硕/博士招生专业为电子科学与技术、材料科学与工程，专硕/博士为电子信息、电子信息材料工程。
+## 师资与科研
+- **师资构成**：现有教师302人，其中教研系139人、科研系95人、教学系14人、实验系21人，教师总数269人，机关33人。
+- **高层次人才**：两院院士2人，领军人才19人，青年人才28人，其他类型人才12人，后备61人。
+- **教师团队**：拥有2个全国高校黄大年式教师团队（电磁辐射与散射教师团队等），2022年获批4个国家自然科学基金创新群体。
+- **科研经费与成果**：近5年科研经费到账稳定在3—4亿元，以纵向项目为主、横向项目为辅；牵头获国家科技奖励11项，近5年发表高水平学术论文2000余篇，申请专利1600余件、授权1300余件。
+- **科研团队**：共20个科研团队，年度经费过千万元的团队15个，其中过亿元团队1个。
+- **科研平台**：拥有国家电磁辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室2个国家级平台，4个国际合作平台，7个省部级科研平台；共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
 ## 电子信息材料与元器件方向
-- **方向内涵**：以电子在物质中的输运特性（电磁声光热力、化学生物等）为基础，涉及电子材料、器件、电路的设计研制生产与应用，以材料为基础、器件为核心、应用为目标导向。
-- **产业背景**：2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍；先进电子材料元器件电路系统等为当前最紧迫的卡脖子问题之一。
-- **应用领域**：电子产品在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域起重要作用，已广泛应用于物联网、移动设备、网络基础设施、无人驾驶、航空航天、医疗健康和可穿戴设备，市场规模达万亿美元量级。
-- **发展趋势**：电子产品向小型化、多功能、低功耗、智能化发展，元器件朝微型化、片式化、集成化、薄膜化、智能化方向演进，强调材料和器件一体化；集成技术结合摩尔定律制程缩小与超摩尔定律功能多样化两条路径。
+- **方向定位**：以电子在物质中的输运特性（电磁声光热力、化学生物等）为基础，设计研究和生产电子器件，以材料为基础、器件为核心、应用为目标导向；概括为「一代材料催生一代器件，服务一代整机」。
+- **产业背景**：2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍；先进电子材料、元器件、电路系统等电子产品是我国目前最为紧迫的卡脖子问题之一，在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域起重要作用，应用规模达万亿美元量级。
+- **发展趋势**：电子产品向小型化、多功能、低功耗、智能化发展，元器件朝微型化、片式化、集成化、薄膜化、智能化方向演进，强调材料和器件一体化；集成技术将摩尔定律制程缩小与超摩尔定律功能多样化相结合。
 - **邓龙江院士团队**：电磁辐射控制材料与技术团队，现有研究人员19人（正高13人、副高15人），近年发表包括Nature在内的论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步奖或技术发明奖二等奖共计3项。
-- **张怀武教授团队**：磁电薄膜与微型器件团队，现有研究人员17人（正高15人、副高2人），重点开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目等100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
-- **国家电磁辐射控制材料工程技术研究中心**：历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级形成国家级平台，主要开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地。
-- **电磁薄膜与集成器件全国重点实验室**：2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建，围绕电子薄膜材料和集成器件开展基础应用与工程应用研究，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向。
-- **研究条件**：科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备或系统500余台套；薄膜材料制备设备50余台套，微纳加工设备30台套（含步进式光刻机、反应离子刻蚀机等），微观表征设备10余台套，材料性能测试设备50余台套。
-- **毕业生去向**：遍布产业界与学术界，包括英特尔、中芯国际、华为、德州仪器及高校科研院所；在读学生杨伟豪以第一作者在Nature Electronics、Nature Communications各发表论文1篇，5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖。
+- **张怀武教授团队**：磁电薄膜与微型器件团队，现有研究人员17人（正高15人、副高2人），重点开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目、国际合作等项目100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
+- **国家级平台**：国家电磁辐射控制材料工程技术研究中心（1990年校级中心起步，经2008年、2013年两次升级形成，开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地）；电磁薄膜与集成器件全国重点实验室（2006年依托新型传感器、功率半导体技术、电子信息材料3个部级重点实验室筹建，围绕电子薄膜材料和集成器件开展研究，形成电子聚合物与阵列传感器、功率半导体与集成技术3个重点方向）。
+- **研究条件**：科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备或系统500余台套；材料制备设备50余台套，微纳加工设备30台套（步进式光刻机、深槽反应离子刻蚀机等），微观表征设备10余台套，材料性能测试设备50余台套。
+- **方向成果与毕业生**：近年每年在Nature及子刊发表多篇重要文章，获国家技术发明奖等共计7项；毕业生遍布英特尔、中芯国际、华为、德州仪器及高校科研院所；在读学生杨伟豪以第一作者在Nature Electronics、Nature Communications各发表论文1篇，5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖，毕业生黄飞获斯坦福大学博士全额奖学金，李凤霞读博期间发表论文16篇（一作6篇），严巍获王大珩光学奖后以优秀青年学者身份加入苏州大学，毕业生万位任河北美泰电子科技公司副总，率先采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术并实现产业化。
 ## 电磁场与微波技术、电路与系统方向
-- **专业构成**：电磁场与微波技术包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
-- **学科历史**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类。
-- **科研团队**：电磁场与微波技术方向由6个团队组成，包括电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
-- **硬件平台**：拥有中国高校最先进的微波暗室群体，以及先进的微波毫米波太赫兹仿真测试平台。
-- **天线与电磁兼容成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能；强耦合超宽带相控阵成果应用于中电14所某大型机载相控阵雷达；电磁测井仪器获国家科技进步二等奖1项，成果在中海油推广应用。
-- **微波毫米波电路成果**：延波教授团队引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委支持，应用于新一代高速通信系统；研制出三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端等微系统成果。
-- **太赫兹成果**：樊勇教授团队研制出0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米；太赫兹通信成果在2023年成都大运会田径项目成功示范应用。
-- **计算电磁学成果**：杨世文教授团队引领的计算电磁学相关算法被评为20世纪十大算法之一。
-- **电路与系统学科概况**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站；拥有教育部国际合作联合实验室、国家高等学校学科创新引智基地，国家级人才4人、新世纪人才2人、教授10人、副教授22人。
-- **电路与系统研究成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制；樊勇教授和张静直（本人）团队研究毫米波通信雷达CMOS芯片；康凯教授团队在毫米波CMOS芯片方向研制超宽带模块级芯片及5G通信和雷达系统。
-- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖；学生获互联网+奖项、国际HPV奖项等；就业领域包括华为、中兴等行业领军企业、各大研究所和高校。
+- **专业构成**：电磁场与微波技术包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向，共同组建射频电子系统的全方位专业覆盖。
+- **学科沿革**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类学科。
+- **研究团队**：电磁场与微波技术方向由6个团队组成——电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
+- **学科平台**：包含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室；硬件平台拥有中国高校最先进的微波暗室群体及先进的微波毫米波太赫兹仿真测试平台。
+- **天线与电磁兼容成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能并提升系统整体性能；在强耦合超宽带相控阵方面取得进展，成果应用于中电14所某大型机载相控阵雷达；在电磁测井仪器方面获国家科技进步二等奖1项，成果在中海油成功推广应用。
+- **毫米波与太赫兹成果**：樊勇教授团队研究毫米波平面集成天线，可应用于毫米波通信雷达系统；研制出0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米；太赫兹通信成果在2023年成都大运会田径项目中成功示范应用。
+- **微波毫米波电路成果**：延波教授团队引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委项目支持，应用于新一代高速通信系统；在固态合成功率源、天线阵列、扩电网络等电路与通信雷达系统方面取得成果；研制出三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端。
+- **计算电磁学与测量成果**：杨世文教授团队引领的计算电磁学算法被评为20世纪十大算法之一；李恩教授团队引领的微波毫米波测量技术突破众多技术封锁，有60多年技术积累和传承；在电磁波与物质互作用机理及测评系统方面面向5G通信、高性能系统、生物医学、新能源等方向提供应用，生物医学电磁学及成像方向发表大量高水平论文并有20余项国家发明专利。
+- **电路与系统学科**：1981年开始招收硕士和博士研究生，1988年成立首批博士后流动站；包含教育部国际合作联合实验室、国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
+- **电路与系统研究成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制，可实现安全可靠实时宽带通信、确保列车安全运行；樊勇教授和张静直（本人）团队研究毫米波通信雷达CMOS芯片，探索集成电路设计新架构；康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统和雷达系统研制成果。
+- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，荣获华为优秀合作项目奖、研究生优秀导学团队提名奖；学生获互联网+奖项、国际HPV各类奖项及优秀论文、创新创业大赛成果奖项；就业领域包括华为、中兴等行业领军企业、各大研究所和高校，毕业生海外留学方面取得不少突破。
 ## 物理电子学方向
-- **学科定义**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学产生新电子器件；典型应用包括微波与电子相互作用形成的微波电子学（微波电真空器件）、光与电子相互作用形成的光电子学（光电器件）。
-- **学科特点**：内容不断充实（如量子电子学内容逐渐增加），学科边界不一定清晰（如光电子学也可属于光学工程一级学科）；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
-- **学校发展历程**：起源于1956年建校时在前苏联专家帮助下成立的电子控器件专业（归属电子器件系）；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年物理电子学院、电工学院和微工学院部分合并成立现在的电子科学与工程学院。
-- **纵向发展**：上游为仿真设计（拥有自主知识产权商用软件MMST和切皮克，并引入人工智能方向），下游为系统应用（用回旋行波管研制毫米波雷达、用行波管做无线输能系统、用磁控管做微波能干燥系统）。
-- **横向发展**：频段从微波上移至毫米波、太赫兹；与医学交叉，利用太赫兹成像提高医学诊断准确性；利用太赫兹宽频带特点做保密通信和高速通信。
-- **科研经费与地位**：每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心；2023年成功举办行业顶级会议；拥有3个四川省工程中心或重点实验室。
-- **团队与学生出口**：物理电子学方向共有9个团队；团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）。
-## 学生视角分享
-- **城市优势**：成都为四川省会、国家中心城市、新一线城市、国家历史文化名城，电子信息产业发达，从英特尔、华为到京东方等巨头汇聚，提供实践平台和就业资源。
-- **学校优势**：电子科技大学是我国电子信息人才培育的代名词，拥有电子信息博物馆（记录我国第一台晶体管收音机诞生），构建了从电子科学与技术、信息与通信工程到集成电路科学与技术的最完整电子信息学科群。
-- **学科实力**：电子科学与技术学科在第4轮学科评估中斩获A+，稳居全国第一；学院拥有四大学科和19个科研团队。
-- **团队情况**：田雨桐所在毫米波技术与系统应用团队负责人为樊勇老师，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，覆盖从芯片、封装、天线、电路、模块到系统的全面知识。
-- **就业情况**：团队硕博毕业生实现100%就业率，就业单位包括各类民营企业、大型央国企和头部科研院所。
-- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金，以及校园地国家助学贷款和生源地助学贷款。
-- **择校建议**：先根据研究方向选择研究团队，再选择导师；可通过学院网站和文献检索网站（如IEEE、中国知网）检索导师论文情况和指导研究生毕业情况，结合兴趣广泛调研。
+- **学科定义**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学中产生新电子器件；典型如微波与电子相互作用形成微波电子学（产生微波电真空器件）、光与电子相互作用形成光电子学（产生光电器件）；学科内容不断充实（量子电子学内容逐渐增加），学科边界不一定清晰（光电子学也可属光学工程一级学科）。
+- **学科特点**：基础性与前沿性并重，数理基础要求高，将物理最新成果应用于电子学具有应用前沿性；物理电子学所生成的电子器件是信息科技产业的重要支撑，是支撑现代信息技术的关键技术学科。
+- **学校发展沿革**：起源于1956年建校时在前苏联专家帮助下成立的电子控器件专业，归入电子器件系；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年由物理电子学院、电工学院和微固学院部分合并成立现在的电子科学与工程学院。
+- **内涵扩展**：纵向发展向上游（仿真设计、数字模拟材料）和下游（系统应用）延伸，拥有自主知识产权的商用软件MMST和切皮克（国内广泛应用的两款算法软件），并将人工智能引入器件设计和电子学应用；系统应用方面研制了毫米波雷达（用回旋行波管）、无线输能系统（用行波管）、微波能干燥系统（用磁控管）。
+- **横向拓展**：频段从微波上移至毫米波到太赫兹；与医学交叉，利用太赫兹成像提高医学诊断准确性，利用太赫兹宽频带特点做保密通信和高速通信。
+- **科研平台与经费**：拥有3个四川省工程中心或重点实验室，参与成立一系列行业协会；每年到校科研经费接近2亿元，为学院最多；是国际世界上最大的真空器件研究中心；2023年成功举办行业顶级会议。
+- **研究团队与出口**：物理电子学方向共有9个团队；团队学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；李天明教授个人每年约2个研究生毕业、1个博士毕业。
+## 学生视角与择校建议
+- **城市优势**：成都是四川省会、国家中心城市、新一线城市、国家历史文化名城、古蜀文明发祥地、中国十大古都之一；电子信息产业发达，英特尔、华为、京东方等行业巨头汇聚，提供实践平台和就业资源。
+- **学校优势**：电子科技大学是我国电子信息人才培育的代名词，拥有电子信息博物馆（记录我国第一台晶体管收音机的诞生），构建了从电子科学与技术、信息与通信工程到集成电路科学与技术的最完整电子信息学科群，走出大批行业领军者与顶尖学者。
+- **学科实力**：电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一；学院拥有四大学科和19个科研团队。
+- **团队培养**：田雨桐所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统5大方向开展研究；研究方向覆盖电磁场与微波技术、电路与系统，可学到从芯片、封装、天线、电路、模块到系统的全面知识；团队硕博毕业生实现100%就业率，就业单位包括各类民营企业、大型央国企和头部科研院所。
+- **校园生活**：2021年跨年学校在主楼前用300架无人机拼出电子科大英文简称UESTC字样。
+- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，奖学金包括国家奖学金、学业奖学金、专项奖学金、新生奖学金及学校和学院设立的其他奖学金，奖助方面有校园地国家助学贷款和生源地助学贷款。
+- **择校建议**：先根据研究方向选择合适研究团队，再选择研究生导师；可从学院网站按兴趣选择团队，再进入团队网页找导师；可通过IEEE Xplore和中国知网等文献检索网站检索导师论文情况和指导研究生毕业情况，结合兴趣广泛调研后选择最合适的研究方向。
 # 各方立场与诉求
-- **主持人**：关注夏令营的具体时间与形式，向段院提出咨询。
-- **段院**：回应称电子学院计划今年举办夏令营活动，但具体时间待定，建议考生和家长加入咨询QQ群（978499108），相关信息将及时在群内发布。
-- **主持人**：补充说明考生和家长可扫码或通过群号加入QQ群进行详细咨询和了解。
-- **主持人**：在直播尾声组织抽奖互动，邀请段院及三位老师共同公布抽奖口令“E生一世，逐梦未来”，并宣布中奖同学可通过私信后台留下联系方式和收货地址领取奖品。
+- **主持人（发言者1）**：开场说明直播因小插曲延迟，随后将时间交给电子科学与工程学院的三位老师介绍学院整体情况；在老师介绍结束后，提示考生和家长如有问题可在弹幕区提出，稍后选取有代表性的问题解答。
+- **段院（发言者2）**：面向考生和家长汇报学院历史沿革、学科设置、师资队伍、科研平台与人才培养成果，强调电子科学与技术为国家重点一级学科，学院拥有2个国家级平台、4个国际合作平台、7个省部级科研平台，近5年科研经费到账稳定在3–4亿元。
+- **柳教授（发言者3）**：介绍电子信息材料与元器件方向，指出中国是电子产品生产大国但尚非强国，2021年集成电路电子产品进口额达2.8万亿元、约为原油进口量的1.7倍，先进电子材料元器件电路系统等是我国目前最为紧迫的卡脖子问题之一；该方向以材料为基础、器件为核心、应用为目标导向，拥有邓龙江院士团队和张怀武教授团队，依托2个国家级平台，毕业生去向包括英特尔、中芯国际、华为、德州仪器等。
+- **张教授（发言者4）**：介绍电磁场与微波技术和电路与系统两个专业方向，涵盖射频微波整套系统的全部研发方向；学科始于1956年由林卫干先生和谢楚芳先生创建，拥有6个研究团队，硬件平台包括中国高校最先进的微波暗室群体；电路与系统学科1981年开始招收研究生、1988年成立首批博士后流动站，连续三年获得全国大学生集成电路创新创业大赛奖项。
+- **李天明教授（发言者5）**：介绍物理电子学学科方向，指出该学科是物理学与电子科学与技术的交叉学科，学校物理电子学起源于1956年建校时的电子控器件专业，经过近70年发展内涵不断扩展，拥有自主知识产权的商用软件MMST和切皮克，每年到校科研经费接近2亿元（为学院最多），2023年成功举办行业顶级会议；团队学生出口约1/3硕博连读、1/3去企业、1/3去研究所。
+- **田雨桐（发言者6，2023级博士研究生）**：从学生视角分享选择电子学院的8个理由，包括成都电子信息产业发达（英特尔、华为、京东方等企业汇聚）、电子科学与技术学科在第4轮学科评估中获A+稳居全国第一、学院拥有四大学科和19个科研团队、团队硕博毕业生就业率100%、奖助体系全覆盖高额度长周期；建议考生先选研究团队再选导师，可通过文献检索网站了解导师论文和指导研究生毕业情况。
+- **主持人（发言者1）与段院（发言者2）**：主持人询问夏令营是否有具体时间和形式，段院回应学院计划今年举办夏令营活动、时间待定，感兴趣的同学可加入QQ群（群号978499108），相关信息届时会及时发布。
 # 达成共识
-- **夏令营安排**：电子学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群及时发布。
-- **咨询渠道**：学院咨询QQ群号确定为**978499108**，考生和家长可扫码或搜索群号加入，进行详细咨询和了解。
-- **抽奖口令**：本场直播抽奖口令为“E生一世，逐梦未来”，中奖同学需私信后台留下联系方式和收货地址，奖品为学校定制马克杯一套。
+- **夏令营安排**：学院计划今年举办夏令营活动，具体时间与形式待定，相关信息将通过学院QQ群（群号978499108）及时发布。
+- **直播互动**：本场直播抽奖口令为「一生一世，逐梦未来」，中奖同学可私信后台留下联系方式和收货地址，奖品为电子科技大学定制马克杯一套（含勺子和杯盖）。
+- **后续沟通渠道**：考生和家长可通过学院QQ群（978499108）进行详细咨询和了解，学院将及时发布夏令营等相关信息。
 # 待协调事项与后续
 ## 待协调事项
-- **夏令营活动**：电子学院计划今年举办，具体时间与形式待定，相关信息将通过QQ群及时发布
+- **夏令营活动**：学院计划今年举办，具体时间与形式待定，段院表示相关信息将及时在QQ群发布
 ## 后续安排与参与方式
-- **咨询QQ群**：978499108，考生和家长可扫码或搜索群号加入，进行详细咨询与了解
-- **抽奖活动**：口令为「E生一世，逐梦未来」，中奖同学可私信后台留下联系方式和收货地址，奖品为电子科技大学整套马克杯（含勺子和杯盖，印有学校logo）
-- **后续沟通**：学院期待在夏令营或研究生入学时与考生和家长进行面对面沟通交流</t>
+- **咨询渠道**：学院QQ群号978499108，考生和家长可扫码或搜索群号加入，进行详细咨询和了解
+- **直播抽奖**：口令为「一生一世，逐梦未来」，中奖同学可私信后台留下联系方式和收货地址，奖品为电子科技大学logo马克杯一套（含勺子和杯盖）
+- **后续活动**：学院期待在夏令营或研究生入学时与考生和家长面对面沟通交流</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>85.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/6643</t>
+          <t>13887/7043</t>
         </is>
       </c>
     </row>
@@ -1403,134 +1397,149 @@
       <c r="C4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次复盘会为2023年度总结暨年终奖颁发会议，由老板主持，围绕年度经营数据、年终奖发放标准、员工评价与颁奖、部门总结及抽奖福利等环节展开。预期目标为总结2023年公司发展状况、公布年终奖并展望2024年。实际结果方面，老板公布年终奖总额226,000元，成本支出（人员工资、外援配音、字幕、租机器）390万元，利润率约24%或27%；最高工资（含年终奖）有2-3人达到20万元以上，平均到手工资1万多元。老板指出成本控制是最大问题，根源在于老板管理不足；公司总量提升、员工收入提升，但成本上升导致结余缩水，老板个人收入比去年少约10万。会议逐一评价员工并颁发最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（市井）、最佳员工奖（游腾宇）、特别贡献奖（李海腾）等五项奖项；各部门总结显示短视频账号粉丝大幅增长但变现重点项目未完成，后期部门加班严重，商务部门实打实项目约300万。
+本次复盘会为公司2023年度总结与年终奖颁发年会，由老板主持，围绕年度经营数据、年终奖发放标准、员工评价与部门总结、颁奖及抽奖等环节展开。预期目标是总结2023年公司发展状况、公布年终奖并展望2024年。实际结果方面，公司年终奖总额为226,000元，成本支出（人员工资、外援配音、字幕、租机器等）390万元，利润率约24%或27%；最高工资（含年终奖）有2-3人达到20万元以上，平均工资到手约1万元。老板指出成本控制是最大问题，根源在于老板管理不足，公司结余缩水，有百来万没收回来，老板承担风险亏了100万。各部门总结显示短视频账号粉丝大幅增长（视频号从700涨到8万，小红书从2000+涨到6.4万，抖音从2000+涨到5.7万，B站从3.1万涨到7.6万），但账号变现课程评分7.5分（满分10分），重点项目未完成；商务部门实打实项目约300万元；后期部门整体技术提升，后半年基本都在加班。老板逐一评价员工并颁发最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李不续）、最佳员工奖（游腾宇）、特别贡献奖（李海涛）等奖项，最后组织抽奖并宣布当日报销福利。
 # 结果与关键成果
 ## 交付与里程碑
-- **年度经营数据公布**：年终奖总额为226,000元；成本支出（人员工资、外援配音、字幕、租机器）390万元；利润率约24%或27%；最高工资（含年终奖）有2-3人达到20万元以上，平均到手工资1万多元
-- **人工支出变化**：2023年平时工资总额提高约25万元，年终奖比去年多13万或12万；干满一年的员工从去年的4-5人增加到今年的12人
-- **公司总量与结余**：公司总量提升、员工收入提升，但成本上升导致结余缩水，到账结余往下跑，另有百来万未收回
-- **老板个人收入**：老板个人收入比去年少约10万元，承担了约100万的亏损风险
+- **短视频账号运营**：2023年视频号粉丝从3月1日的719人增长至8万，小红书从2000+增长至6.4万，抖音从2000+增长至5.7万，B站从3.1万增长至7.6万；涨粉转折点为6月20日第一条外出拍摄的对话视频。
+- **账号变现**：课程变现评分7.5分（满分10分），其中1分期待空间、0.5分期待值；重点项目变现未完成。
+- **直播**：视频号直播4-5场（含新年场），平均在线人数5000+，前100人平均在线时长50分钟以上；因暂无课程，尚未实现直播变现。
+- **商务部门业绩**：实打实项目约300万元，若计入入围等项目则更多。
+- **后期部门交付**：2023年项目整体劳累程度比去年差、种类比去年多，后半年基本都在加班，但项目未做砸过，甲方满意度整体尚可。
 ## 数据与指标
-- **视频号**：粉丝从3月1日的719人增长至8万，涨粉起色始于6月20日第一条外出拍摄的对话视频
-- **小红书**：粉丝从1月的2000+增长至6.4万
-- **抖音**：粉丝从2000+增长至5.7万
-- **B站**：粉丝从3.1万增长至7.6万
-- **账号变现**：课程变现评分7.5分（满分10分），其中0.5分为期待空间；变现重点项目未完成
-- **直播**：视频号直播4-5场，平均每场在线人数5000+，前100人平均在线时长50分钟以上
-- **商务部门**：实打实项目约300万元，加上入围等应更多
+- **年终奖总额**：226,000元。
+- **成本支出**：人员工资、外援配音、字幕、租机器等实打实支出390万元。
+- **利润率**：约24%或27%，老板认为非常不可观。
+- **员工收入**：最高工资（含年终奖）2-3人达到20万元以上；平均工资到手1万多元。
+- **人工支出变化**：平时工资总额比去年提高约25万元；年终奖比去年多13.12万元。
+- **人员留存**：干满一年的员工从去年的4-5人增加到今年的12人。
+- **公司结余**：总量提升但成本上升，结余到账缩水，另有百来万未收回；老板承担风险亏了100万。
 ## 制度与流程
-- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元，今年约1000元；干满一年以一个月基本工资为基准，表现好可更高；干得久且满意，预算可达大几万，实际拿到的一般为两三万
-- **个人年终奖数额**：不一一公布，以发到手为准
-- **奖项评选机制**：共6人5项奖，评选有竞争性，同级别框出2-3人，2选1或3选1；最佳新人奖含鼓励成分，后期三项奖完全出于肯定
-- **颁奖侧重**：年终奖及奖项对后期有所侧重，是老板唯一愿意解释的原因；拍摄人员收入不会比后期少
+- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元，今年约1000元；干满一年以一个月基本工资为基准；干得久且满意可给大几万预算，实际拿到2-3万左右。
+- **个人年终奖不一一公布**：老板决定不公布个人数额，以发到手为准。
+- **奖项评选机制**：共6人5项奖，评选有竞争性，同级别框出2-3人后2选1或3选1；最佳新人奖含鼓励成分，后期三项奖完全出于肯定。
+- **颁奖侧重说明**：年终奖与奖项对后期部门有所侧重，是老板唯一愿意解释的发放原因；拍摄人员收入不会比后期少，已掌握平衡。
 ## 团队与人员
-### 红叶子
-- **综合评价**：入职两三个月（10月入职，11月转正），政委给予非常高评价，认为很难招到既懂技术又懂英语、有把事情做好的精神头的人才
-- **工作态度**：填工资表时在意见栏认真写如何把项目做得更好的建议
-### 郭东辉
-- **综合评价**：干满一年的运营，非常有经验，克服了本不应面对的困难；老板表示公司可能限制了他的发挥，应表示歉意
-- **账号运营**：负责多平台运营，6月20日前潘老师曾10次提醒其出去找工作，郭东辉坚持不放弃，说服潘老师外出拍摄后账号起色
-### 刘腾宇
-- **综合评价**：评价最高，职业性、专业性、纪律性均为最好；按时完成交付，问题倒来倒去倒不到他头上；沟通专业，对客户回复得体
-- **客户反馈**：宁波城市项目客户罗峰向政委表示「如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了」
-- **年终奖**：刚满一年但给老板感觉像干了5-6年的老员工，年终奖会让人惊喜，可能翻倍
-### 欧阳小元
-- **综合评价**：刚满一年，工作态度认真，技术水平有学习能力，进步明显；沟通能力需再爬坡
-- **获奖**：获最佳进步奖
-### 徐艺玲
-- **综合评价**：干得稍久的员工，一遍过的次数非常多，仔细认真挑不出毛病；技术层面有进步，原先只能剪课程，今年剪宣传片类也像模像样
-- **客户认可**：杨晶项目其他人做不了，徐艺玲做完后客户说「你还是让那个小姑娘来做」
-### 张文倩
-- **综合评价**：编导岗位，综合能力强（沟通+专业），表现高出老板期待；宁波等难活本以为干不了但完成了
-- **待提升**：因年龄和工作年限，经验与职场老人有差距
-### 市井
-- **综合评价**：后期技术标杆，最好的没有之一；品质上依然最高
-- **获奖**：获后期独挡一面奖，能完美胜任课程、微电影、MV、快剪等各类后期
-### 钱德峰
-- **综合评价**：元老级人物，后半年拍摄密集，两个月连轴转没有一天休息；除拍摄外还安排拍摄人员，操心较多
-- **额外贡献**：主动建议办停车券、设备更新等运营层面事项，非本职工作但关心公司发展
+### 红叶子（入职两三个月，10月入职、11月转正）
+- **综合评价**：政委给予非常高的评价，认为很难招到既懂技术又懂英语、有把事情做好的精神头的人才；在工资表意见栏会写如何把项目做得更好的建议。
+- **奖项**：获最佳新人奖。
+### 郭东辉（运营，干满一年）
+- **综合评价**：非常有经验的运营，克服了本不应面对的困难；老板表示公司可能限制了他的发挥，应表示歉意。
+### 游腾宇（后期，刚满一年）
+- **职业性**：对老板和客户回复都非常专业，沟通能力强。
+- **纪律性**：几乎没有迟到，请假严格按规定提前告知并安排好工作。
+- **技术反馈**：宁波城市项目客户罗峰反馈「如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了」；重要活安排给游腾宇后老板可完全放心。
+- **效率与质量**：效率最高且不会出问题，做得好。
+- **奖项**：获最佳员工奖，奖金稍多；年终奖在既定标准上因林海腾肯定再拉一档，老板称会让人惊喜、可能翻倍。
+### 欧阳小元（刚满一年）
+- **工作态度**：认真，技术水平能力过关，学习能力强，有进步。
+- **提升空间**：沟通能力需再爬坡。
+- **奖项**：获最佳进步奖，技术进步明显跑了一截。
+### 徐艺玲（干得稍久的员工）
+- **工作质量**：一遍过的非常多，仔细认真，挑不出毛病；技术层面有进步，原先只能剪课程，今年剪宣传片类也像模像样。
+- **客户反馈**：杨晶项目其他人做不了，她做完后客户说「还是让那个小姑娘来做」。
+### 张文倩（编导）
+- **综合评价**：灵光，综合能力强（沟通+专业），表现高出老板期待；宁波等老板以为干不了的活也完成了。
+- **提升空间**：因年龄和工作年限，经验与职场感觉有所欠缺。
+### 市井（后期技术标杆）
+- **技术评价**：依然是公司最好的后期，没有之一；能胜任更高品质的工作。
+- **参与项目**：尊重个人意见，必要的后期会议有参加。
+### 钱德峰（元老级，拍摄）
+- **工作强度**：后半年拍摄密集，两个月连轴转没有一天休息；回到公司很晚又要开车去很远的地方。
+- **额外贡献**：安排拍摄人员、建议办停车券、关注设备更新，非本职工作但关心公司发展。
+- **提升空间**：期待更强的执行能力（项目、沟通谈判）。
 ### 徐武安
-- **综合评价**：灵光、眼里有活，驻场警察学院孤苦伶仃非常辛苦；拍摄技术水平好于后期技术水平
-- **客户反馈**：刚去时被认为经验欠缺，后来反馈「挺灵的」
-### 宋俊逸
-- **综合评价**：入职两三个月，编导职位；第一个宁波两分钟宣传片任务，发来文稿后老板觉得「行家一出手便知有没有」，效率高
-- **交付情况**：监狱、财经等项目未出现任何问题，交给其完全放心
-### 张扬
-- **综合评价**：公司邀请来的人才，来了半年左右，职业态度和工作能力有目共睹，基本达到期待；老板认为2023年最有价值的事就是招其进来
-- **获奖**：获最佳新人奖
-### 林海腾
-- **综合评价**：对运营层面有重要作用，上传下达；后期安排是繁重的活
-- **获奖**：获特别贡献奖，奖金为单项奖中最多；辛苦程度最大，半夜或周末被侵占最多，负责救火、沟通协调
-### 李国宇
-- **综合评价**：干满一年，拍摄水平在公司算较高，能胜任稍高难度工作；后期有灵性，能听懂指导
-- **待提升**：沟通能力需加强
-### 张启
-- **综合评价**：干了一年的商务，表现高于预期；以为害羞实际外向，有主观能动性，主动联系客户打电话
-- **支持情况**：老板支持较少，几乎没什么项目，后续会考虑给予更多支持
+- **综合评价**：灵光、眼里有活；去警察学院驻场一人孤苦伶仃，客户从起初认为经验欠缺转为觉得挺灵；拍摄技术水平好于后期技术水平。
+### 宋俊逸（编导，入职两三个月）
+- **综合评价**：第一个活是宁波两分钟宣传片，发来文稿后老板觉得「行家一出手便知有没有」，效率不错；后续监狱、财经等项目未出现任何问题，交给完全放心。
+### 张扬（入职半年）
+- **综合评价**：公司邀请来的人才，职业态度和工作能力有目共睹，基本达到期待；老板称2023年干到最有价值的事就是把他招进来。
+- **奖项**：获最佳新人奖。
+### 林海腾（运营层面）
+- **综合评价**：对运营层面有重要作用，上传下达，传达员工声音；后期安排工作繁重。
+- **奖项**：获特别贡献奖，奖金为单项奖中最多；因辛苦程度最大（半夜、周六周日被侵占最多、最操心、执行层面救火、上传下达）。
+### 李国宇（拍摄，干满一年）
+- **拍摄水平**：公司内算比较高，能胜任稍高难度的活。
+- **后期能力**：有灵性、能进步能听懂；剪理工项目第一遍乱七八糟，被逼一顿后完美交差。
+- **提升空间**：沟通能力需提升。
+### 张启（商务，干满一年）
+- **综合评价**：表现高于老板预期，外向、有主观能动性，会主动联系客户打电话；老板支持较少，几乎没什么项目，后面会考虑给更多支持。
 ## 年度总结、奖项与福利
-- **最佳新人奖**：颁给红叶子、张扬，各含红包
-- **最佳进步奖**：颁给欧阳小元
-- **后期独挡一面奖**：颁给市井，政委搜了好久名字，为独有奖项
-- **最佳员工奖**：颁给刘腾宇，含金量最高，老板与政委认真讨论、达成一致
-- **特别贡献奖**：颁给林海腾，奖金为单项奖中最多
-- **证书制作**：皮质证书40元一本（含设计费），字体认真校对，不掉色掉粉
-- **抽奖福利**：15个奖品，含充电宝（价值约180元）、观影券（价值30元）、洗头膏（价值七八十元，未寄到）；老板另写了一个100元红包的奖
-- **报销福利**：当天看电影或吃饭在一定额度内可报销，仅限当天
+- **年度总结**：2023年公司总量提升，员工拿到钱提升，成本也往上跑（负值）；公司结余到账往下跑，有百来万没收回来，稍微缩水。
+- **颁奖仪式**：今年认真对待仪式感（去年李海腾建议公司欠缺仪式感），证书为皮质、40元一本含设计费，字体认真对过；另有两个洗手包未寄到（值七八十元）。
+- **奖项设置**：共6人5项——最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李不续）、最佳员工奖（游腾宇）、特别贡献奖（林海腾）。
+- **抽奖福利**：15个奖品，含充电宝（价值79元）、观影券（价值30元）、洗头膏（价值七八十元）、老板自写100元红包奖。
+- **报销福利**：当天看电影或吃饭在一定额度内可报销，仅限当天有效；不报销则来年补饭。
+- **加班补贴**：年终奖中考虑加班因素，补贴约一两千元。
 # 亮点事项
-## 账号运营突破与坚持
-- **粉丝量级跃升**：视频号粉丝从3月1日的700人增长至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，**全部平台自6月20日第一条外拍对话视频起出现转折**。
-- **破局关键动作**：运营郭东辉在潘老师先后**10次**提醒放弃该项目的情况下坚持不放弃，以破釜沉舟的心情极力说服潘老师到室外拍摄，恰逢新同事加入，项目得以延续并实现增长。
-- **直播初步验证**：视频号直播4-5场，平均在线人数达5000+，前100名观众平均停留50分钟以上，为后续变现打下基础。
-- **外部认可佐证**：同行运营者（卖虾、卖螃蟹的商家）对团队能坚持这么久表示惊讶，认为按常规状况早该放弃。
+## 短视频账号突破性增长
+- **粉丝数大幅跃升**：视频号从3月1日的700粉丝增长至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，各平台均实现数倍至百倍级增长。
+- **关键转折点**：6月20日第一条外出拍摄的对话类视频成为涨粉起点，此前潘老师已10次提醒运营人员考虑放弃该项目。
+- **成功原因**：运营人员以破釜沉舟的心态极力说服潘老师尝试外出拍摄，恰逢新同事加入，项目得以坚持并突破；运营人员坚持"如果要放弃应由老板决定而非自己放弃"的信念。
+- **数据驱动决策**：运营人员每晚8-9点抽一小时刷竞品英语老师直播间（侃哥、巧克力、克瑞斯金等），研究内容与互动方式，所有内容决策均有数据支撑而非凭空设想。
+- **外部认可**：同行运营者（卖虾、卖螃蟹的商家）对团队能坚持这么久表示惊讶，认为这种状况下多数人会放弃。
 ## 员工表现超出预期
-- **刘腾宇获最高评价**：老板称其为评价最高、没有之一，职业性、专业性、纪律性俱佳；客户（宁波城市项目）反馈「如果不是你这个小姑娘做得好，你们做得这么慢，早投诉你们了」；重要活安排给刘腾宇后老板可直接放心遗忘；因林海腾大力肯定，年终奖在既定标准上**再拉一档**，老板预计「可能还会翻倍」。
-- **红叶子获政委高度评价**：政委（平时相对严苛）评价「很难招到这样的一个人才，既懂技术又懂英语，而且有把事情做好的精神头」，在工资表意见栏主动写如何把项目做得更好。
-- **张扬获老板最高认可**：老板称「2023年干到最有价值的一件事就是把他招进来」，其职业态度与工作能力基本达到期待，且能做三维（往年二维三维均外包），段位让人惊喜。
-- **宋俊逸首活即证能力**：入职两三个月，老板安排宁波两分钟宣传片，文稿发来后老板判断「这个人是对的」，后续监狱、财经等项目未出任何问题，完全放心。
-- **张文倩完成高难度项目**：老板原以为宁波类项目可能黄掉，但张文倩完成且超出期待，被认为综合能力（沟通+专业）要求高的岗位做得「出乎意料」。
-- **欧阳小元获最佳进步奖**：技术进步「明显跑了一截」，老板强调「进步不是所有人都有的」，并寄语保持热爱与好奇。
-## 仪式感建设与激励创新
-- **首次正式颁奖**：增设最佳新人奖、最佳进步奖、后期独挡一面奖、最佳员工奖、特别贡献奖共5项6人，源于去年李海腾建议公司欠缺仪式感；老板称今年**非常认真对待**，奖项评选经与政委认真讨论，2选1或3选1竞争性评选。
-- **证书细节用心**：皮质证书40元一本（含设计费），老板亲自核对字体，选用「苍耳青和」字体，明确要求不掉色掉粉。
-- **年终奖总额提升**：年终奖总额226,000元，比去年多13万或12万；干满一年员工从去年4-5人增至今年12人；最高收入（含年终奖）2-3人达20万以上，平均到手工资1万多元。
-- **加班补贴纳入考量**：与政委商量年终奖时，对后半年高强度加班（含晚上、周末）在年终奖基础上**再补贴一两千元**，作为对辛苦的认可。
-## 成本优化意识萌芽
-- **内部拍摄可行性被提出**：钱德峰指出部分外援工作（如简单按机位、保证机器不关机）公司内部即可完成，但「连这样的人公司都凑不出来」；外援拍摄与内部人员拍摄**两边价格差很多**，建议后期人员尝试参与拍摄，既提升收入也增加体验。
-- **老板回应并定调**：认可拍摄性价比高，未阻止任何人参与，期待明年大家都能参与拍摄，称这对个人市场价值也是提升。
+- **游腾宇获最高评价**：老板称其为"评价最高的，没有之一"，职业性、专业性、纪律性均最佳——迟到几乎没有，请假严格按规定提前告知并安排好工作；客户反馈良好，宁波城市项目客户表示"如果不是你这个小姑娘做得好，你们做得这么慢，早投诉你们了"；重要活安排给游腾宇后老板便不再操心。因林海腾大力肯定，年终奖在既定标准上**额外拉高一档**，老板称"刚满一年的员工却给人干了5、6年老员工的错觉"。
+- **张扬获高度认可**：老板称"2023年干到最有价值的一件事就是把他招进来"，其职业态度与工作能力基本达到期待，公司给予了有诚意的待遇；老板明确表示"有这样的态度或能力的员工如果还出现问题，那就是老板或制度管理沟通的问题"。
+- **红叶子获政委极高评价**：政委（以严苛著称）评价"很难招到这样的一个人才，既懂技术又懂英语，而且有把事情做好的精神头"，在工资表意见栏会认真写如何把项目做得更好的建议。
+- **宋俊逸首秀即证明能力**：入职两三个月，老板安排第一个宁波两分钟宣传片任务，很快交回文稿，老板评价"行家一出手便知有没有"，后续监狱、财经等项目均未出问题，"交给他是完全放心的"。
+- **张文倩超出老板预期**：老板原以为宁波等较难项目可能做不成，已做好心理准备，但张文倩均能完成，"出乎我的意料"。
+- **新员工带来技术惊喜**：张扬（音）能完成三维制作，而往年二维三维均外包，有望内部解决此类需求。
+## 后期团队整体能力跃升
+- **技术分级模糊化**：后期人员之间原本明确的分级今年模糊了，效率整体接近，制作能力整体提升，林海腾表示"不怎么需要我额外操心"。
+- **高强度下保质保量**：后半年基本都在加班，晚上、周末均如此，但质量未下降；林海腾评价"有怨言但还会接着干，这是一种职业操守"。
+- **年终奖体现认可**：老板与政委商量年终奖时，考虑到加班情况，在既定标准外**额外补贴一两千元**。
+## 仪式感建设成效显著
+- **首次正式颁奖**：增设最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李不续）、最佳员工奖（游腾宇）、特别贡献奖（李海涛）共5项6人，奖项评选经认真讨论，2选1或3选1竞争产生。
+- **证书用心制作**：皮质证书每本40元含设计费，老板亲自核对字体（选用苍耳青和），明确要求不掉色掉粉。
+- **回应员工建议**：仪式感缺失是去年李海腾（音）及员工提出的建议，今年认真对待并落实。
 # 不足事项
-- **成本控制极差**：2023年实打实花出去的钱（含人员工资、外援配音、字幕、租机器）达390万元，利润率仅约24%或27%，老板直言“非常不可观”。根因：**老板对成本关心或关注不够，不够雷厉风行，出现问题没有及时解决**，老板自认“最大的癌症的问题，根源的问题就是老板的问题”。
-- **公司结余缩水**：虽然总量提升、员工收入提升，但成本往上跑，公司结余到账往下跑，且还有百来万没收回来，实际结余“稍微缩水”。根因：成本上升幅度超过总量提升带来的结余空间。
-- **老板个人收入下降**：老板自述“我们每个人会比去年少拿个10万块钱左右”，且公司承担了亏损100万的风险。根因：成本控制不力叠加未收回款项，压缩了老板个人收益。
-- **账号变现重点项目未完成**：短视频账号粉丝大幅增长（视频号从700涨到8万，小红书从2000+涨到6.4万，抖音从2000+涨到5.7万，B站从3.1万涨到7.6万），但账号变现课程评分仅7.5分（满分10分），老板明确“重点项目的话可以说是没有完成”。根因：账号起步艰难，6月20日之前老板曾10次提醒运营“出去找工作”，项目差点放弃；变现能力尚未建立，直播虽场均5000+人但“没有课程，所以说他是可以进行变现的”尚未落地。
-- **加班严重、休息时间被侵占**：后期部门后半年基本都在加班，晚上、周末都在赶工，很少正常休息。根因：**人不够是最大因素**——老板承认“没有及时招更合适或更合适人数的人员来做这个事儿”，商务业务断断续续产生，给人“不需要招这么多人”的错觉，但平时积累的人脉资源又不确定，导致判断失误。
-- **外援成本高但内部无人可用**：拍摄请了大量外援，成本很高，但部分工作公司自己人内部就可以搞定（如“上午谁有空谁去一下，按个机位，只要让机器不关机就ok”），实际“这样的人我们公司都凑不出来”。根因：后期人员活多且忙，抽不出人手；老板也承认部分外援是“我们技术水平达不到”所致。
-- **拍摄与后期收入不平衡**：老板明确“拿到了钱，其实后期要比前期少一截的”，且年终奖和奖项“侧重于后期”。根因：老板主观意志决定，但承认这是“唯一愿意解释的一点”，希望员工理解。
-- **员工拒绝拍摄安排**：老板指出安排拍摄时，有员工直接说“我没空”，老板认为“这个是非常不职业的”。根因：员工缺乏职业意识，老板要求“如果领导问到你应该起码解释一下我手头上忙的东西，或者说你勉为其难安排一下”。
-- **商务部门支持不足**：老板承认“我们做老板来说，给他的支持比较少，他几乎没有什么项目，我们就帮他聊了聊，或者是帮着他走走打理”。根因：老板对商务部门“给予的支持，或者管理或者是关心其实是不够的”，明年会反思这个问题。
-- **员工自我评价未达预期**：后期员工自述“2023年就是我自己对我自己的预期的话，我感觉年终对我自己来说，我感觉是没达到我自己的预期的”，原因包括效率、时间、项目上对同事和甲方的沟通做得不太好。
-- **个别员工沟通吃力**：张文倩反映法院项目“虽然是做完了，但是我同学跟他们沟通上会比较吃力”，因为对方“总是在踢皮球”，标准不明确。
+## 成本控制与经营风险
+- **成本控制非常差**：2023年实打实花出去的钱（人员工资、外援配音、字幕、租机器等）达390万元，利润率仅约24%或27%，老板明确表示这是公司最大的问题；若没有增量支撑，今年这个状况下年会都不会开。
+- **公司结余缩水**：总量在提升、员工拿到钱在提升，但成本也在往上跑，公司结余到账是往下跑的；还有百来万没收回来，实际结余稍微缩水。
+- **老板承担亏损风险**：老板个人亏了100万，并明确表示即使拿得少也比员工拿得多，风险由老板顶着。
+- **根因——老板管理不足**：老板自认这是最大的癌症问题，根源在于**老板对业务关心或关注不够，或不够雷厉风行，出现问题没有及时解决**；明年开会时再讨论成本控制问题。
+## 短视频账号运营
+- **账号尚未变现**：短视频账号虽粉丝大幅增长（视频号从700涨到8万、小红书从2000+涨到6.4万、抖音从2000+涨到5.7万、B站从3.1万涨到7.6万），但账号变现重点项目**没有完成**，课程变现评分7.5分（满分10分），其中0.5分是期待空间。
+- **直播尚未形成变现闭环**：视频号直播4-5场，平均在线人数5000+，但**现在没有课程，所以尚不能进行变现**。
+- **6月20日前项目濒临放弃**：在6月20日外出拍摄视频起色之前，潘老师已多次（约10次）提醒运营人员出去找工作、项目不想干了；运营人员认为不应由自己放弃，坚持到说服潘老师外出拍摄后项目才出现转变。
+- **公司限制部门发展**：老板承认合作对象和公司可能限制了短视频部门的发展，对部门员工表示歉意，并给予一定补偿。
+## 人员与加班
+- **加班严重、人员不足**：后期部门后半年基本都在加班，很少正常休息，晚上、周末都被占用；老板承认这是**判断失误——没有及时招合适或足够数量的人员**，商务业务断断续续给人不需要多招人的错觉，但平时积累的人脉资源又不确定，导致人不够成为加班最直观的因素。
+- **外援成本高、内部参与不足**：拍摄外援费用与内部人员拍摄价格相差很多，但公司内部凑不出人去按个机位、保证机器不关机；员工反映喊人拍摄时很多人以没空、很忙、不想去为由推脱。
+- **年终奖侧重后期**：老板明确年终奖和奖项发放侧重后期部门，后期比前期少一截是事实，但即使侧重后期，拍摄人员也不会比后期少，老板表示这是唯一愿意解释的发放原因。
+## 员工个人表现未达预期
+- **李国宇沟通能力待提升**：老板评价其拍摄水平较高、后期有灵性，但更高期待是沟通能力，并直言「你也有问题，而且很严重」。
+- **欧阳小元沟通能力需爬坡**：老板肯定其工作态度、技术水平与学习能力，但认为沟通能力可能要再爬坡会好一点。
+- **张文倩经验欠缺**：老板肯定其综合能力与灵光性，但因年龄和工作年限问题，从经验或感觉上相比职场老人有所欠缺。
+- **张文倩法院项目沟通吃力**：张文倩自述法院项目虽做完，但同学沟通上比较吃力，对方总在踢皮球，不清楚标准该怎么做。
+- **徐艺玲状态不佳**：老板多次表示感觉其不开心、板着脸，但本人未明确回应原因；老板对其更高期待「明年再说」。
+- **张扬问题明年再说**：老板表示张扬基本达到期待、是2023年最有价值的一次招聘，但也直言「你问题也很严重，具体问题明年再说」。
+- **张启项目支持不足**：老板承认商务方面给张启的支持比较少，他几乎没有什么项目，老板只是帮着聊了聊或打理，后面会考虑给更多支持和帮助。
+- **李国宇自评未达预期**：李国宇自述2023年对自己预期未达到，包括效率、时间方面，以及项目上对同事和甲方的沟通做得不太好。
 # 改进计划
 ## 成本控制与经营改善
-- **针对成本控制差、利润率仅24%或27%的问题**：老板表示明年开会时再讨论成本控制事宜，未给出具体方案或责任人。
-- **针对公司结余缩水、有百来万未收回的问题**：老板提及有百来万未收回，但未给出明确的回款计划或时间表。
-## 管理改进
-- **针对老板管理不足、对员工关心或关注不够、不够雷厉风行、出现问题未及时解决这一成本问题的根源**：老板明确表示明年会反思这个问题，并计划给予员工更多的支持、管理和关心。
-- **针对商务部门支持不足的问题**：老板表示后面会考虑给商务部门员工（如张启）更多的支持和帮助，包括协助洽谈项目。
-## 拍摄与人员安排
-- **针对外援成本高、部分拍摄工作内部人员即可完成但无人手的问题**：钱德峰建议尝试让公司内部人员参与拍摄，以提升收入并体验工作；老板回应称期待大家都能参与拍摄，明年会往这个方向靠，希望每个人都能参与。
-- **针对员工以「没空」等理由拒绝拍摄安排的问题**：老板指出直接说「没空」非常不职业，要求员工在领导询问时应解释手头工作或勉为其难安排，此事项明年再议。
-## 短视频账号发展
-- **针对短视频账号尚未变现的问题**：老板表示明年期待账号能开始变现，并会投入更大的精力、给予足够的重视。
-## 后期部门工作负荷
-- **针对后期部门加班严重、人不够是最大因素的问题**：老板承认未及时招聘合适或足够人数的人员是判断失误，但未给出明年的具体招聘计划或人数目标。</t>
+- **针对成本控制差、利润率仅24%或27%的问题**：老板表示明年开会时再讨论成本控制的具体方案，未给出具体措施。
+- **针对公司结余缩水、有百来万没收回来的问题**：老板承认承担风险亏了100万，但未给出追收或止损的具体计划。
+- **针对老板管理不足这一成本问题的根源**：老板自述对工作关心或关注不够、不够雷厉风行、出现问题未及时解决，明年会反思这个问题。
+## 短视频账号变现与运营
+- **针对短视频账号尚未变现的问题**：老板期待明年账号能开始变现，并承诺投入更大精力、给予足够重视。
+- **针对账号运营中说服与坚持困难的问题**：运营郭东辉总结认知收获为“最大的敌人是自己”，坚持把事情做下去，未给出具体改进动作。
+## 人员配置与加班问题
+- **针对后半年加班严重、人员不足的问题**：老板承认是判断失误——商务来活断断续续，误以为不需要招更多人，但平时积累的人脉资源又不确定，导致未及时招合适人数；未给出明年补员的具体计划。
+- **针对外援成本高的问题**：员工钱德峰提出公司内部人员可承担部分简单拍摄（如按个机位、保证机器不关机），与请外援价格差很多，建议尝试内部拍摄；老板回应期待大家都能参与拍摄，明年会往这个方向靠，希望大家至少能应付。
+- **针对员工直接说“没空”不参与拍摄的不职业现象**：老板指出被领导问到时应解释手头工作或勉为其难安排，不能直接拒绝。
+## 部门协作与支持
+- **针对商务部门项目支持少的问题**：老板表示张启做项目时老板支持较少，几乎没给项目，后面会考虑给予更多支持和帮助。
+- **针对后期部门工作繁重、休息时间被侵占的问题**：老板期待明年能更多进行组织协调，提高效率、提升工作开心程度，尽可能少侵占大家休息时间。
+- **针对员工沟通能力提升空间**：老板对欧阳小元、李国宇提出沟通能力需再爬坡的期待，未给出具体培养措施。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/6443</t>
+          <t>24562/7233</t>
         </is>
       </c>
     </row>
@@ -2073,100 +2082,76 @@
       <c r="C5" t="inlineStr">
         <is>
           <t># 全文摘要
-本次专项讨论会由办事处组织，业主代表、业委会工作组与物业方就小区服务问题及业主大会召开事宜进行协调。业主方列举10条长期未解决的服务问题（入户门柱灯、水系、监控、绿化、围墙、民生配套、雨水倒灌、人员配备等），要求召开业主大会表决物业去留；物业方逐条回应，称资金困难、部分问题属地产责任，并宣布本月起诉业委会。双方未达成一致，业主方决定正常推进业主大会。物业方称业主欠费170多万，回款40万可修部分问题；年收入100来万，人工成本100多万，每年亏损；部分问题属地产前期配套或红线外责任，地产公司已申请破产。业主方认为服务不达标导致拒缴，形成恶性循环，并称可能集体起诉要求返还部分物业费；物业方称起诉期间无法更换物业公司。
+本次专项讨论会由办事处组织，业主代表、业委会与物业方就小区服务质量、物业费欠费、业主大会召开及物业去留等矛盾进行协调。业主自发接龙约200名业主支持召开业主大会，业委会坚持推进业主大会表决，物业方则质疑程序合法性并称已启动法律程序，双方未达成一致。业主代表列举小区10条问题，涵盖门柱灯未开、水系未开启、监控损坏、监控室无人值班、绿化死亡、围墙缺口、民生配套缺失、雨水倒灌、人员配备不足等；物业方逐条回应，称部分属地产责任、费用不足等。物业方称业主欠费170多万，要求先回款40万再维修，并称年收入100多万、人工成本100多万，每年亏损，地产公司已申请破产。业主方认为物业服务无滞后性，应先改善服务再谈缴费，并称物业经理曾威胁不交费就上门吃饭。最终双方未达成一致，业主方决定继续推进业主大会表决换物业，物业方决定本月起诉业委会。
 # 分段速览
 ## 00:10-05:37 开场与费用问题讨论
-会议开场，发言者2与发言者1、发言者3就小区供暖开户费、配套费缴纳情况展开讨论。发言者2指出园区从建设到后期从未验收，开户费应由地产出资并将管道交接给供暖公司，但至今未完工，导致责任归属不清。发言者3确认相关费用已交清，发言者2补充称开发商将费用交入其公司，具体去向不明。发言者2还提及业主退费、工资比例等话题，但表述零散，未形成明确结论。
-## 05:37-10:14 业主诉求与物业现状
-发言者4提出业主买房满怀希望、不愿退房，发言者2回应称一期结算时按平方点计算，二期补助可达29%。发言者2提到有热心业主自发组织收费，涉及3万元及400元费用，但未推进。发言者4补充称二期三期交费业主合计约20来户。发言者2表示物业费收缴不足50户难以维持运营，并提及配电室三级管理问题，强调需坦诚相待、共同商量解决。
-## 10:14-14:28 业委会成立与群组情况
-发言者2强调成立业主委员会应保持良好态度、不暴露敌对情绪，任何人不应有私心。发言者4介绍小区业主自发组织接龙，约200名业主支持召开业主大会，并指出业委会或业主无权单方面撤换物业，需业主大会表决。发言者2询问工作群数量，发言者4回应称业委会工作组仅一个群，准业主分5个群，筹备组6人各联系一部分；最早的业主群由老邱哥建立，已有5、6年历史。
-## 14:28-17:53 业主大会程序讨论
-发言者2质疑接龙程序，认为讨论需有明确结果，不应失控。发言者5总结接龙业主心声：一是要求整改小区存在问题，二是整改不了则考虑更换物业，原物业也可参与投标。发言者5提及业主群中列出11个问题。发言者2强调召开业主大会前应与物业公司沟通，但物业方未接到任何通知，认为接龙有组织性，物业方未参与议题制定。
-## 17:53-21:23 物业方宣布起诉
-发言者2郑重声明，鉴于双方存在违法情况，已与集团法务沟通，本月将正式起诉业委会，并称欠费人员不能成为业主代表。发言者2表示已在业主群掌握证据，上午与高级人民法院、滨城区人民法院均有沟通记录，将起诉业委会及保洁业主代表，起诉过程可能影响个人经营。
-## 21:23-30:53 业主列举10条问题
-发言者4逐条列举小区长期存在的问题：①入户门柱灯从未开启；②内部水系从未开启；③售楼处迎宾水系从未开启；④监控几乎全部损坏，上月进贼未获取数据；⑤监控室24小时值班及一键直达功能荒废；⑥绿化维护不足，去年死树多棵；⑦北边围墙用烂铁皮遮挡且有缺口，存在安全隐患；⑧快递柜、直饮水机、宽带、暖气开通等民生问题无进展；⑨雨水倒灌问题自2019年存在未解决；⑩物业人员从办公室近10人减至4人，维修人员从5人减至2人。
-## 31:22-38:01 物业方逐条回应
-发言者2逐条回应：①门柱灯因能耗成本过高无法运营，业委会曾承诺支持缴费后修复；②水系存在严重质量问题，属地产配套未完成；③监控维修因费用超出运营承担，园区年收入100来万、人工成本100多万，每年亏损；④监控画面已第一时间提供给警方；⑤绿化问题因业委会10月才成立，冬季无法更换；⑥北边围墙属红线以外且涉及违建官司，物业无责处理；⑦民生配套属地产前期配套；⑧雨水倒灌属地产设计问题；⑨人员配备不足因地产补亏款未结账。
-## 38:53-46:14 双方争执激化
-发言者4反驳称物业服务无滞后性，问题从交房至今一直存在，并非物业方近期资金困难才出现。发言者2坚持走法律程序，称诉讼期间无法召开业主大会。发言者4表示会议无继续必要，基本决议是换掉物业，并称业委会成立之日已自动解除物业合同关系。发言者2要求先结清费用，双方就围栏定制、半热带安装等承诺未兑现问题争执。
-## 46:59-53:01 恶性循环与反诉表态
-发言者3指出无钱无法整改、业主不愿缴费形成恶性循环，区领导也难以解决。发言者4提出可能集体起诉要求返还部分物业费。发言者8质疑物业窥探业主隐私，表示将反诉。发言者7称已与集团法务沟通，业主群动态已截屏留证。发言者5建议业主大会开与不开都应推进，需与物业打招呼明确议题。
-## 53:01-01:03:16 调解失败与会议结束
-发言者3建议双方冷静、向好的方向发展，物业应拿出真实行动赢得业主认可。发言者7表示公司入不敷出，业主欠费170多万，回款40万可修部分问题，地产公司已申请破产。发言者3指出服务好是缴费前提，矛盾越积越深更难解决。发言者4表示将正常推进业主大会，发言者2称会议未解决实质性问题，双方未达成一致，会议结束。
+会议开场后，发言者2首先谈及小区供暖开户费问题，指出园区自建设至今从未验收，开户费本应由地产出资并将管道交接给供暖公司，但至今未完工、未验收，导致多数人误认为是物业责任。发言者3确认相关配套费已交清，发言者2补充开发商已交至其公司，但具体去向不清楚。发言者2还提到业主自发组织收费，涉及三个月或四个月的费用，有热心业主参与，一批人涉及13万元，并提及23年收费问题。发言者4表示业主们买房满怀希望，不愿意退房，希望问题能够解决。
+## 05:37-10:05 业主诉求与物业问题初现
+发言者4指出业主们不愿退房、希望问题解决。发言者2提到一期管理时按平方点结算，二期应补助约29%，但推进受阻。发言者4说明二期三期加起来交钱的业主约20来户。发言者2谈到物业费收缴困难，50户中仅达到10户，达不到要求则物业不提供服务。发言者4表示自己家里热了但管道少。发言者2分析20、30户业主中，小部分想今年解决供暖，更大部分担心管道问题影响明年使用。发言者2还提到配电室分三级，需要一级一级排查才能解决。
+## 10:05-14:28 业委会成立与群组情况
+发言者2强调成立业主委员会应坦诚相待、不暴露敌对情绪，希望大家把好的态度放在一起共事，任何人不要有私心。发言者4介绍前一段时间业主自发组织接龙，约200来个业主参与，主要议题是想召开业主大会，并指出业委会或业主个人都无权决定撤换或开除物业，只有业主大会能表决。发言者4建议尽快召开业主大会让全体业主表决。关于群组情况，发言者4说明业委会工作组只有一个群，准业主分了5个群，共6个群；发言者5补充筹备组成立时6个人各联系一部分业主；最早的业主群是老邱哥建的，从交房开始已有5、6年。
+## 14:28-18:01 业主大会程序与议题讨论
+发言者2质疑接龙程序，认为没有经过讨论就形成结论不妥。发言者5总结接龙业主的心声：第一是要求开会，第二是要求小区存在的问题整改，若整改不了再考虑更换物业，原物业也可以投标参与招标。发言者5提到群里反映的问题有11个。发言者2强调召开业主大会或组成决议前，事先应与物业公司沟通，但物业未接到任何通知，也未参与接龙组织，质疑接龙是有组织的行动。
+## 18:01-22:08 物业方宣布起诉
+发言者2郑重声明，鉴于双方存在包括成立之初和工作过程中的违法情况，已与集团法务沟通，本月将正式起诉。发言者2指出欠费人员不能成为业主代表，顶名也不能成为业主代表，将依法追究责任。发言者2称已在业主群掌握很多证据和依据，欠费周期超过一年的业主将被起诉，上午9:52已与高级人民法院通电话，也与滨城区人民法院沟通，将起诉业委会及保洁业主代表。发言者2提醒起诉过程可能影响个人经营。发言者5表示业主大会开与不开是必须的事，今天先讨论问题能否改善。
+## 22:08-31:22 业主列举十大问题
+发言者4逐条列举小区问题：①入户庭院门柱灯从未开启；②内部水系从未开启，业主加价购买水系旁房产；③售楼处门口迎宾水系从未开启；④监控几乎全部损坏，上个月进贼时110派出所和刑警大队均未从监控获得数据；⑤监控室从交房起应24小时有人值班，门铃有一键直达功能，但王艳芳上任后此服务荒废；⑥绿化维护缺失，去年死了很多树，小区门口就死了三棵，物业管家称要等明年看能否发芽；⑦北边围墙用烂铁皮遮挡，最西边有缺口，任何人都可自由进出，物业拆除铁皮后承诺定制围挡但至今未装，经证实根本没定制；⑧民生附属问题如快递柜、直饮水机、宽带覆盖、暖气开通开户等多年无进展，最终由业委会全程办理；⑨雨水倒灌问题自2019年起造成业主财产损失，多次反映无解决方案；⑩物业人员配备严重不足，办公室从近10人减至4人，维修人员从5人减至2人。
+## 31:22-38:53 物业逐条回应
+发言者2逐条回应：①门柱灯未亮是因能耗成本物业无法运营，曾与业委会沟通，业委会承诺支持缴费并协助收费，收上费用后拿出一部分修复；②水系从交付起存在严重质量问题，泵无法运转，属地产配套未完成，由地产维修，不属物业责任；③④监控损坏因费用超支，物业从进入园区起年收入100来万，光人工成本就100多万，不包括垃圾清运费、能耗、维修、税费等，每年亏损，可公开查账；⑤民警进园区时物业第一时间将拍摄画面截取给派出所和刑警，有照片和记录；⑥绿化死亡问题，业委会今年10月才成立备案，之后是冬季，换树责任无法承担；⑦北围墙属红线以外，涉及法律官司且属违建，物业有权不处理，曾协调施工单位定做但因费用太高未成，此事与业委会沟通不下5次；⑧民生配套属地产前期配套，后期开通费用由业主承担；⑨雨水倒灌是地产前期设计和建设问题，排水量超出承载范围；⑩人员配备不足因地产补亏款未结，项目20来人一年成本100多万，今年维修费花了几十万。
+## 38:53-46:14 双方激烈交锋
+发言者4反驳物业服务没有滞后性，全滨州小区没有必须先收钱再服务的先例，指出门柱灯、水系、监控等问题从交房起就存在，是时序性问题。发言者2强调今天来是协调业委会成立问题，并非要求换物业。发言者4表示已无讨论必要，基本定下召开业主大会、决议换掉物业，建议当场表决。发言者2称起诉期间无法更换物业公司。发言者4称业委会成立之日即自动解除与物业的合同关系。发言者4还提到物业曾承诺定制围栏但拿不出证据，刘主任现场布置装保温带任务物业也未办。发言者4表示仅代表个人意见，但99%的业主支持换物业，并提到此前业主喝茶被监视。
+## 46:14-53:01 欠费循环与起诉争议
+发言者3指出问题陷入死循环：业主因整改未完成不愿交物业费，物业没钱无法整改，情况越来越糟。发言者4提出业主可能集体起诉物业，要求返还交房以来未达标服务的物业费。发言者7确认上午已给求助人打电话，又给集团法务打电话，集团法务今天操作手续，已与法院沟通，群里动态已截屏保存。发言者8质疑物业窥探业主隐私，表示只要物业起诉就反诉。发言者4指责物业经理在进贼时第一句话是"你交物业费了吗"，还说过"你不交物业费我们就上你家吃饭"，发言者7要求拿出录音证据，双方争执不下。
+## 53:01-01:03:16 调解无果与会议结束
+发言者8提到筹备组起就有热心业主被造谣说给物业当会计，表示可拿身份证去查。发言者3建议物业拿出真实行动赢得业主信任，指出小区三天两头停水停电、院墙问题、雪未清理等。发言者7称业主欠物业公司170多万，要求先回款40万用于维修，并称地产公司已申请破产，无法追讨。发言者3反问既然地产能把物业带进来，为何不能把地产签回来。发言者7表示已与地产沟通不下五六遍甚至十遍，地产已申请破产。发言者2总结今天结果不好，隔阂越来越深，未解决实质性问题。发言者4表示将正常推进业主大会，不再与物业协商。
 # 要点梳理
 ## 业主大会召开与表决
-- **业主接龙**：小区业主自发组织接龙，约200名业主支持召开业主大会，主要议题为讨论小区问题及物业去留。
-- **群组结构**：业委会工作组仅1个群，准业主分5个群，共6个群；筹备组6人各联系一部分业主。
-- **接龙群来源**：接龙群为交房时即建立的业主自发群，已存在5、6年，群主为老邱哥。
-- **业主方主张**：业委会或业主个人无权决定撤换物业，须通过业主大会由全体业主表决；建议尽快召开业主大会。
-- **物业方程序质疑**：物业方称召开业主大会前须事先与物业公司沟通，但未接到任何通知，对议题内容不知情、未参与。
-- **物业方诉讼声明**：物业方称已与集团法务沟通，本月将正式起诉业委会，起诉期间业主可能无法行使表决权。
-- **欠费业主资格**：物业方称欠费人员不能成为业主代表，顶名者也不能，将依法追究责任。
-- **业主方决定**：业主方表示将正常推进业主大会，不受物业方起诉影响；物业方称诉讼期间无法更换物业公司。
-## 小区服务问题清单
-- **入户门柱灯**：每家每户入户庭院门柱灯自交房以来从未开启过，业主认为属应得服务未兑现。
-- **内部水系**：业主加价购买水系旁房产，但内部水系自卖房后从未开启过一次。
-- **迎宾水系**：售楼处门口迎宾水系从未开启，业主认为系小区门面，水亦象征财。
-- **监控损坏**：监控几乎全部损坏，上个月小区进贼，110派出所及刑警大队均未从监控获得任何数据。
-- **监控室值班**：交房时配备监控室24小时值班，门铃有一键直达功能，可紧急处理；王艳芳上任后此服务荒废，监控室无人值班。
-- **绿化维护**：绿化维护严重不足，去年死树多棵，小区进门两侧已知死树3棵；业主报修门口病树，物业管家称经理回复等明年看能否发芽长叶。
-- **北边围墙**：小区围墙围上后，北边一直用烂铁皮遮挡，最西边有缺口，社会人员可随意进出；业委会责令整改后物业拆除铁皮，但未再安装，曾称已定制围挡，业主证实并无定制。
-- **民生配套**：快递柜、直饮水机、宽带覆盖、暖气开通开户等民生问题多年无进展，业主多次询问无果，最终由业委会全程办理。
-- **雨水倒灌**：自2019年起每逢大雨雨水倒灌，业主均有不同程度财产损失，多次向物业反映要求完整解决方案，至今无进展。
-- **人员配备**：物业办公室最初近10人，现含经理仅4人；维修人员从5人减至2人；门卫、保洁等人员配备严重不足。
-## 物业方逐条回应
-- **门柱灯**：灯未亮系园区能耗成本过高、物业公司无法运营所致；物业曾与业委会沟通，业委会承诺支持全员缴费并协助收费，收上费用后拿出一部分修复。
-- **水系问题**：水系自交付起存在严重质量问题，所有泵无法正常运转，属地产配套未完成，由地产维修，不属于物业责任。
-- **监控维修**：监控损坏因无费用、超出运营承担；物业公司年保护收入100来万，20多人人工成本100多万，不含垃圾清运费、能耗、维修、税费及办公成本，每年亏损，可公开查账。
-- **监控画面**：警察进入园区时，物业第一时间将拍摄画面截取给派出所和刑警，有刑警调取监控的照片和记录；对业委会所称未拍到监控的信息来源提出质疑。
-- **绿化死亡**：业委会成立于今年10月，备案亦在10月，此后为冬季，非更换绿化季节，更换后死亡责任无法承担。
-- **北边围墙**：北边围墙在物业服务范围红线以外，且涉及法律官司、本身属违建，物业有权不处理；物业曾协调施工单位定做，因费用太高未成，费用本应由物业承担，已与业委会沟通不下5次。
-- **民生配套**：宽带、快递柜、燃气等属地产前期配套，按建设条例和前期配套要求应由地产负责；后期开通物业可协助，费用由业主承担。
-- **雨水倒灌**：园区地势四周高中间矮，车库设计为向内斜坡向下，属地产前期设计和建设是否符合规范的问题，超出物业解决范围。
-- **人员配备**：前期人员充足系地产给了一批补亏款，该款至今未结账；现项目20来人，年成本100多万，今年维修费已花几十万。
-## 物业费与资金问题
-- **欠费金额**：物业方称业主欠物业费170多万，回款40万即可解决部分问题，但账上一分钱没有。
-- **经营亏损**：物业方称年保护收入100来万，人工成本100多万，每年亏损，今年亏损额度拉大；地产公司已申请破产。
-- **业委会引导拒缴**：物业方称业委会成员当面承诺协助缴费，背后却在业主群告知大家不要缴费，相关记录已留存，将走法律程序，以阻碍经营、造成经济损失为由起诉。
-- **业主方观点**：物业服务没有滞后性，全滨州小区没有先收钱再服务的先例；问题系交房以来时序性存在，非物业方来后才出现。
-- **业主方反诉意向**：业主方提出在最终解决前，可能集体起诉要求返还自交房以来未达标服务对应的部分物业费。
-- **恶性循环**：发言者3指出，服务不整改业主不愿缴费，不缴费物业没钱、服务更差，形成恶性循环，区领导、市领导来也难解决。
-## 法律诉讼与反诉
-- **物业方起诉决定**：物业方称已掌握业主群内证据和依据，上午9:52与高级人民法院通话，并与滨城区人民法院沟通，本月正式起诉业委会，包括保洁业主代表。
-- **起诉理由**：物业方称业委会从选举即存在违法行为，后期决策及在业主群煽动均不符职责，另有撬门行为；以阻碍正常经营、造成经济损失为由起诉。
-- **业主方反诉**：业主方称物业窥探业主隐私，只要物业起诉即反诉并拿出证据。
-- **诉讼影响**：物业方称起诉过程可能影响业委会成员个人经营；案件存续期间无法更换物业公司。
-- **业委会合同主张**：业主方称业委会成立之日即自动解除与物业的合同关系。
-## 现场争执与调解
-- **物业经理言论争议**：业主方称进贼时联系物业经理，对方第一句即问「你交物业费了吗？没交物业费不给你服务」，并称「不交物业费上你家吃饭去」；物业方要求拿出录音，业主方称物业经理已承认「上你家吃饭」。
-- **调解建议**：发言者3建议物业拿出真实行动赢得业主信任，双方互相体谅，避免矛盾激化；物业方称已多次明确表态，业主欠费100多万，要求回款40万即修部分问题。
-- **物业方态度**：物业方称公司现状运营困难，不止一次与业委会沟通并留存录像；发言者7称「心里不想去了」，但强调群内信息均已知晓。
-- **业主方态度**：发言者4称已无调解必要，物业不承认遗留问题、不会解决，基本决议为换掉物业；发言者5称99%业主支持其个人看法。
-- **会议结果**：发言者2称今天结果不理想，矛盾隔阂越来越深，未解决实质性问题；发言者3建议办事处再努力协调，双方都是为了工作，没必要把个人牵扯进来。
+- **业主接龙**：业主自发组织接龙，约200名业主支持召开业主大会，主要议题为讨论小区问题及物业去留。
+- **群组构成**：业委会工作组仅1个群，准业主分5个群，共6个群；接龙群为交房时即建的业主群，已存在5-6年。
+- **物业质疑程序**：物业方称未接到任何事先沟通，业主群内发接龙属有组织行为，议题不明；称欠费超一年业主不能成为业主代表，顶名者也不能。
+- **物业宣布起诉**：物业方称已与集团法务沟通，本月将正式起诉业委会，理由是选举及决策存在违法行为、在业主群煽动、阻碍正常经营造成经济损失。
+- **业主方立场**：业委会成员表示无权决定撤换物业，但业主大会可表决；坚持推进业主大会，表决物业去留。
+- **表决权争议**：物业方称诉讼期间无法更换物业公司；业主方称业委会成立之日即自动解除物业合同关系，双方各执一词。
+- **会议结论**：双方未达成一致，业主方决定继续推进业主大会，物业方将依法起诉。
+## 小区问题清单与物业回应
+- **门柱灯未开启**：业主称入户庭院门柱灯从未开启；物业称因能耗成本无法运营，曾与业委会沟通，承诺收齐费用后拿出一部分修复。
+- **内部水系与迎宾水系**：业主称水系自交房从未开启，业主加价购买水系旁房产；物业称水系存在严重质量问题，泵无法运转，属地产配套未完成，已由地产维修，非物业责任。
+- **监控损坏**：业主称监控几乎全部损坏，上个月小区进贼，110派出所及刑警大队未从监控获得任何数据；物业称已第一时间将拍摄画面截取给派出所和刑警，并出示刑警调取监控的照片和记录。
+- **监控室服务**：业主称交房时监控室应24小时有人值班，门铃有一键直达功能，但王艳芳上任后服务荒废；物业未直接回应。
+- **绿化死亡**：业主称去年大量树木死亡，小区门口光已知就死3棵，向物业管家反映时被告知「经理说了，明年看看能不能发芽」；物业称业委会今年10月成立备案，之后为冬季，换树死树责任无法承担。
+- **北围墙缺口**：业主称北边用烂铁皮遮挡，最西边有缺口，社会人员可随意进出，业委会责令整改后物业拆除铁皮再无动作，哄骗业主已定制围挡；物业称北围墙属红线以外、涉及违建官司，不在物业服务范围，曾协调厂家定做但因费用太高未成，费用需物业承担，已与业委会沟通不下5次。
+- **民生配套缺失**：业主称快递柜、直饮水机、宽带覆盖、暖气开通开户等多年无进展，最终由业委会全程办理；物业称按建设条例和前期配套要求属地产前期配套，后期开通费用由业主承担。
+- **雨水倒灌**：业主称2019年起每户均有不同程度财产损失，多次反映无解决方案；物业称园区地势四周高中间矮，车库设计为斜坡向下，属地产前期设计和建设问题，超出物业解决范围。
+- **人员配备不足**：业主称物业办公室由近10人减至4人，维修人员由5人减至2人；物业称因地产补亏款未结账，现项目20来人，年人工成本100多万。
+## 物业费与经营状况
+- **物业经营数据**：物业称园区年物业费收入100来万，人工成本100多万，不含垃圾清运费、能耗、维修、税费及办公成本，每年亏损，可公开查账。
+- **业主欠费**：物业称业主欠费170多万，要求先回款40万用于维修，账上一分钱没有；业主方认为物业服务无滞后性，应先改善服务再谈缴费。
+- **业委会引导拒缴**：物业称业委会成员当面承诺帮物业收费，背后却在业主群告知大家不要缴费，已有记录，将以此起诉阻碍经营。
+- **地产公司破产**：物业称地产公司已申请破产，无法追讨配套费用；业主方质疑「申请破产就没有办法了吗」，物业称业委会可集体提出。
+- **物业经理言论争议**：业主称物业经理曾对业主说「你不交物业费，我们上你家吃饭去」；物业方要求业主拿出录音，业主称「上我家吃饭」一事物业经理已承认。
+- **恶性循环**：业主方指出服务不整改→业主不愿缴费→物业没钱→服务更差，形成恶性循环，区领导、市领导也难以解决。
 ## 结论与决定
-- **业主方决定**：正常推进业主大会，由全体业主表决物业去留；业主方表示物业可起诉，业主方按自身流程推进。
-- **物业方决定**：本月正式起诉业委会，以阻碍正常经营、造成经济损失为由；已与集团法务及高级人民法院、滨城区人民法院沟通。
-- **未达成一致**：双方就业主大会能否在诉讼期间召开、物业费欠费与服务质量责任归属、物业合同是否自动解除等问题未达成一致。
+- **物业方决定本月起诉业委会**：以选举违法、煽动业主、阻碍正常经营造成经济损失为由，已与集团法务及滨城区人民法院、高级人民法院沟通（上午9:52致电高院），本月正式起诉。
+- **业主方决定继续推进业主大会**：业委会表示将按流程召开业主大会，由全体业主表决物业去留；物业方称诉讼期间无法更换物业，业主方称业委会成立之日即自动解除物业合同关系。
 ## 行动项与分工
-- **物业方**：本月内完成起诉手续，集团法务今日操作相关手续。
-- **业主方**：正常推进业主大会召开流程。
-- **物业方**：可公开查账，供业主核实经营收支情况。
+- **物业方**：本月内完成对业委会的起诉手续，集团法务今日操作。
+- **业主方**：继续推进业主大会召开及表决程序。
+- **办事处（发言者3）**：建议物业拿出真实行动赢得业主信任，呼吁双方互相理解、避免矛盾激化。
 ## 待确认与风险
-- **业主大会召开受阻风险**：物业方起诉可能导致诉讼期间业主大会无法召开，双方对此存在分歧。
-- **欠费与服务恶性循环**：业主欠费170多万，物业无资金维修，服务不改善则业主更不愿缴费，矛盾持续加深。
-- **治安风险**：北边围墙缺口未封闭、监控几乎全部损坏，社会人员可随意进出小区，上月已发生进贼事件。
-- **雨水倒灌风险**：问题自2019年未解决，明年大雨可能再次造成业主财产损失。
-- **隐私争议**：业主方质疑物业窥探业主隐私，物业方称已截屏留存业主群动态作为证据，双方将进入诉讼程序。</t>
+- **业主大会能否在诉讼期间召开**：双方对法律程序理解不一，物业称案件存续期间无法更换物业，业主方称无法律条文禁止则照常召开。
+- **物业费欠费与维修资金**：物业要求先回款40万再维修，业主方坚持先整改再缴费，双方未达成一致。
+- **小区问题整改责任归属**：水系、雨水倒灌、民生配套等物业称属地产责任，但地产公司已申请破产，配套问题无法解决。
+- **围墙缺口安全隐患**：北围墙缺口致社会人员随意进出，上个月进贼后仍未修复，业主担心过年安全。
+- **监控损坏取证风险**：监控几乎全部损坏，上个月进贼时警方未从监控获得数据，治安事件无法取证。
+- **物业起诉影响**：起诉可能影响业委会成员个人经营，双方对立情绪加剧，调解空间缩小。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>75.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/5566</t>
+          <t>21511/5504</t>
         </is>
       </c>
     </row>
@@ -2415,84 +2400,81 @@
       <c r="C6" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌论坛由发言者2主持，围绕具身智能领域的关键技术问题展开，多位嘉宾与博士生参与讨论。发言者2代表多模态大模型与具身智能融合方向，并介绍雄辉（于洋老师博士生，强化学习方向）、薛寒（卢策武老师博士生，数据收集与柔性物体操作方向）、志龙（于洋老师博士生，具身模型与世界模型方向）等博士生参与。研讨旨在探讨具身智能的大模型架构、硬件形态、世界模型定义、策略学习路线及数据采集等核心议题，各方观点碰撞，未形成统一结论。
-- **具身智能大模型架构**：讨论端到端模型与分层模型（如固定前段加Action refiner）的优劣，以及大模型是否应从感知到控制全链路统一。
-- **具身智能硬件形态**：探讨具身智能的物理载体最终收敛为人形机器人还是特种机器人形态，以及硬件对算法发展的支撑与期待。
-- **世界模型的定义与实现路径**：讨论强化学习领域与计算机视觉领域对世界模型的不同理解，以及是否需要三维归纳偏置、是否应统一模型。
-- **强化学习与模仿学习的路线之争**：探讨未来策略学习最终路线是强化学习、模仿学习还是两者混合，以及各自在数据、仿真、落地方面的瓶颈。
-- **数据采集与仿真数据**：讨论真机数据与仿真数据的成本、质量与规模化路径，以及互联网视频数据、可穿戴设备、无标注数据等新数据来源的可行性。
-- **国产仿真系统**：探讨中国具身智能仿真是否强依赖英伟达生态，以及国产替代产品的可能性。
+本次圆桌论坛由发言者2主持，围绕具身智能领域的关键技术问题展开研讨，参与方包括多位学界与业界嘉宾及博士生。发言者2代表多模态大模型与具身智能融合方向，并介绍雄辉（于洋老师博士生，强化学习方向）、薛寒博士（卢策武老师博士生，数据收集与柔性物体操作方向）、志龙（于洋老师博士生，具身模型世界模型方向）等博士生参与。研讨旨在探讨具身智能大模型与硬件形态、世界模型定义与实现、强化学习与模仿学习路线、数据采集与仿真等议题，各方观点碰撞，未形成统一结论。
+- **具身智能大模型与硬件形态**：探讨具身智能的最终形态收敛方向，以及大模型与硬件之间的协同关系，涉及人形机器人、特种机器人、软硬件协同优化等核心问题。
+- **世界模型的定义与实现**：讨论强化学习领域与计算机视觉领域对世界模型的不同理解，涉及可交互性、物理规律、三维表征、inductive bias等关键问题。
+- **强化学习与模仿学习的路线**：探讨具身智能策略学习的两大主流流派——强化学习与模仿学习——的优劣与融合方式，涉及数据效率、仿真环境依赖、落地可行性等核心痛点。
+- **数据采集与仿真**：讨论真实数据与仿真数据的采集方式、质量保障与比例搭配，涉及数据视角控制、标定、柔性物体仿真、可穿戴设备采集、无标注数据利用等议题。
 # 核心观点
-## 硬件形态与模型收敛
-- **发言者3（机械领域视角）**：提出具身智能硬件形态的收敛问题——是像人一样的人形机器人，还是像科幻片中可变形的大方块；机械领域存在「机械智能」思路，如软手通过强摩擦和顺应性，在抓取误差较大时仍能抓牢。
-- **发言者4（博士生）**：硬件需高寿命与高可靠性；具身智能训练中模型预测失误易导致机器人撞桌损坏，现有工业机械臂并非为此设计，需要个人柔顺的硬件结构以支持大规模真机评估的scale up。
-- **发言者2（主持人）**：具身智能是软硬件协同优化的范式；以松灵两代产品为例，第二代在遥操与策略部署上明显优于第一代；与任老师合作的凝胶夹爪可反馈触觉、增加摩擦力，体现协同进化。
-- **发言者5（嘉宾）**：若大模型从上到下直通，会消除硬件迭代的可能性——新硬件（如软体机器人）出现时大模型需完全重新训练；模型至少应分大脑与小脑两层，大脑不变、小脑adaptive到肢体（以手断后大脑仍能指挥右手泡咖啡为例）。
-- **发言者6（嘉宾）**：从第一性原理出发，人形机器人因现实环境（桌椅等）为人而设计必然存在，可能是双足或轮式并配灵巧手（引马斯克采访：公司花一半精力做22自由度灵巧手）；特种机器人在工业制造中已大量存在（车厂、微电子制造厂机械臂实现97%以上自动化），两类将并存。
-- **发言者7（嘉宾）**：从产业角度预测具身智能融资将经历四波——第一波后过完年进入低谷，第二波接近自动驾驶融资规模，第三波接近大模型规模，第四波接近互联网规模；每波技术变革将深刻改变具身大模型硬件与云端模型形态，时间取决于技术突破。
-## 世界模型的定义与实现路径
-- **发言者8（博士生，强化学习视角）**：世界模型概念可回溯至1990年强化学习之父Sutton的Dyna-Q文章，本质是黑盒、输出下一时刻观测，第一要义是**可交互**（最终目的是学策略）；2018年Schmidhuber与杨立昆定义的世界模型含表征与转移两个组件；当前世界模型在物理规律体现上欠缺明显，希望引入3D、触觉等多模态信息完善。
-- **发言者7（嘉宾，CV视角）**：CV界共识是计算机视觉发展多年就是为了动态重建物理世界，可作为RL世界模型的被调用工具；但三维CV技术栈深，RL博士生难以完全学习，导致RL领域不太关注三维表征——这是学术发展阶段导致的现状。
-- **发言者7（嘉宾）**：提出数据规模与归纳偏置（inductive bias）的权衡——数据足够多时需要的归纳偏置变少，数据少时需要的更多；以ImageNet、GPT的成功说明大规模学习可不需要归纳偏置，以UniSim说明当前仍需3D归纳偏置；学术发展呈螺旋前进，世界模型是否需要3D归纳偏置最终由数据决定。
-- **发言者5（嘉宾）**：以游戏主角跳楼与真人cosplay为例——两者观测完全相同但结局不同（游戏稳落地、现实死亡），世界模型无法同时acquire两个dynamics，因这是完全歧义的问题；**世界模型可能无法统一（应是多个），但policy有可能统一**，因为人作为同一policy既能玩游戏也能在现实中避免跳楼。
-- **发言者9（嘉宾）**：提出反对意见——强化学习的世界模型是任务导向的，目标只是更好学策略（产生latent state或reward即可），CV世界模型做得足够好可用于强化，但为解强化任务未必需要；针对发言者5的歧义问题，提出不同物理结构可有相同统一表征、policy能识别condition则world model也能识别的反例。
-- **发言者5（嘉宾）回应**：加condition后问题变成复杂度权衡——M个独立世界模型 vs 一个高维可控condition的世界模型，从可实现角度M个模型更简单；目前没有atari game能靠一个world model建模所有游戏；policy可通过更长的observation窗口隐式体现condition，但用GPT模型回归atari games大概率是强记。
-## 强化学习与模仿学习的路线之争
-- **发言者10（业界嘉宾）**：公司采用模型强化加机理融合方式；监督学习在具身任务中动作空间大、数据分布远不足以支撑高维动作，强化学习强依赖仿真环境、纯RL路线难以做到sim-to-real迁移；需将RL的决策空间与任务设定（state-action对）做很好限定，如上层RL做决策、底层用MPC或DWA等传统方法执行，实际部署中能提升整体性能。
-- **发言者9（嘉宾）**：同意混合方式，不认为收敛到最后强化或模仿能单独完成；复杂问题历史规律都是先模仿后强化（如AlphaStar、GPT）——from scratch跑强化样本复杂度不可接受，人类模仿提供的先验信息没有坏处；单独模仿不行（人类行为不一定最优解，需强化达到superhuman），单独强化也不行（除非任务足够简单）。
-- **发言者5（嘉宾）**：PID控制必有反馈（无反馈做不了控制），因此凡PID能做的系统必然有反馈，可完全拿该反馈作为强化学习执行过程中的reward；过去用PID效果不够好，现在通过强化做得更好。
-- **发言者11（嘉宾）**：模仿学习与强化学习并不冲突——学人类运动先验可用基于强化学习的DeepMind Motion Matching，也可用模仿学习；有现成数据就从模仿学习角度做，没有数据（如复杂运动）就先用RL获取再以BC形式建模latent；有了latent后完成任务可通过RL快速找到对应latent。
-## 数据采集与仿真数据
-- **发言者11（嘉宾）**：数据质量关键在于视角控制与标定——Open X等数据集融合多家数据、相机视角无法固定，而视角非常影响policy表现；手眼标定看似已解决但至今仍有人在发文章、解决得不好；Open X等数据集只捕捉本体信息（末端、关节角度、力矩），缺少物体运动，OpenLink从采集出发必须记录物体运动（当时设备有限只能采集刚体和关节体）。
-- **发言者4（博士生）**：all in真实数据采集路线；柔性体操作（叠衣服、系鞋带、拉拉链）现有仿真需IPC等先进图形学技术、算力要求高且掌握者少（如UCLA蒋正凡夫），进展缓慢；真实数据是相对低成本方案——「真实世界本身就是最好的仿真器」。
-- **发言者4（博士生）**：现有采集方式难以scale——派林收集1万小时数据，即使融资再多一两个数量级也达不到GPT-2、GPT-3级别；终极形态可能是脑机接口或机电方式无感采集多模态数据，现阶段可通过可穿戴设备在人们日常做事时采集；互联网视频数据与机器人所需数据差异大——网上教叠衣服的视频都是平铺状态，但机器人见到的是从洗衣机拿出揉成一团的状态，人类习以为常的简单事恰恰是机器人最缺的数据。
-- **发言者2（主持人）**：互联网数据在数据金字塔最底层、质量低——本人受ego4d数据集「毒害」，清洗耗时三个月；仿真数据可弥补真实数据不足——300条仿真数据训出的策略直接去真实世界成功率很低，但300条仿真数据加20条真机数据成功率显著提升（用很原始的fine-tune方法）；仿真数据可包含物体随机位置、随机orientation、任意初始状态。
-- **发言者7（嘉宾）**：真实数据还是仿真数据应case by case看成本——室内服务机器人真机数据收集有可行性，但自动驾驶corner case让人去「鬼探头」太危险；**提出2025年应迈向大规模利用无标注真实数据**（如segment anything、depth anything），不再讨论真实与仿真有标注数据的比例问题（1:9、2:8、5:5等观点已过时）。
-- **发言者7（嘉宾）**：国产仿真系统是产业问题——宋应等团队赌会被卡脖子、做国产替代，business by business是很好的生意；技术上最终会比较统一，但business上很复杂，取决于是否脱钩卡脖子。
+## 具身智能大模型与硬件形态
+- **发言者3（机械与传感器方向）**：提出具身智能形态收敛问题，认为可能像人形机器人，也可能像科幻片中可变形的大方块（如《星际穿越》），机械领域关注"机械智能"，如软手通过强摩擦和顺应性在较大误差下仍能抓牢物体。
+- **发言者5**：认为大模型不应从上到下统一为一个模型，至少应分两层——大脑不变、小脑适应肢体；以人手断后仍能泡咖啡为例，说明底层控制模型（小脑）需适应构型变化，而大脑无需更换。
+- **发言者6**：从第一性原理出发，认为人形机器人与特种机器人将并存——人形机器人因现实环境为人设计而存在（如马斯克公司投入一半精力做22自由度灵巧手），特种机器人已在车厂、微电子制造厂实现97%以上自动化。
+- **发言者7（产业视角）**：预测具身智能融资将经历四波——第一波后进入低谷，第二波达自动驾驶融资规模，第三波达大模型规模，第四波达互联网规模；每波技术变革将深刻改变本体形态与云端模型形态，当前10亿人民币融资规模相比整个市场仍很小。
+- **发言者4（博士生）**：对硬件提出期待——需要寿命长、可靠性高，现有工业机械臂未考虑具身智能实验需求，模型预测撞桌几次即损坏，难以scale up，需要个人柔顺硬件结构支持大规模真机evaluation。
+- **发言者2（主持人）**：认为具身智能是软硬件协同优化的范式，以松灵两代产品对比说明硬件迭代提升策略部署效果，凝胶夹爪可反馈触觉且摩擦力更好。
+## 世界模型的定义与实现
+- **发言者8（博士生，强化学习方向）**：强化学习领域世界模型第一要义是可交互——回溯至1990-91年Sutton的Dyna-Q文章，世界模型是黑盒、输出下一时刻观测；其次是物理规律体现，当前世界模型在此方面欠缺明显；最后才是引入3D信息或触觉等多模态感知。
+- **发言者7（CV方向）**：CV领域世界模型追求动态重建物理世界，可作为RL中世界模型的工具，但当前技术仍粗糙；三维CV技术栈深，RL博士生难以完全掌握，导致RL领域不太关注三维表征；提出"data bias trade off"第一性原理——数据多时需要的inductive bias少，数据少时需要的多，如UniSim需要3D inductive bias，但数据scaling up后可能不需要。
+- **发言者5**：认为世界模型可能无法统一——以游戏主角跳楼与真人跳楼为例，相同观测输入对应不同dynamics输出，是完全歧义的问题；但policy可以统一，因为同一大脑可在游戏中跳楼、在现实中避免跳楼；世界模型应是多个，policy可以是一个。
+- **发言者9**：提出反对意见——强化学习的世界模型是任务导向的，只要能更好学策略即可，不一定需要CV式的完整世界模型；针对发言者5的歧义问题，提出不同物理结构可有相同统一表征，但承认M个独立模型比一个高维可控condition模型更简单可实现。
+- **发言者7**：总结RL与CV对world models关注点不同——RL更端到端，CV更关注解耦表征，这是学术发展阶段导致的现状；历史上inductive bias与大规模学习呈螺旋前进状态，90年代朱松纯引入复杂inductive bias，ImageNet时代大规模学习更重要，现在又进入需要inductive bias的阶段。
+## 强化学习与模仿学习的路线
+- **发言者10（业界嘉宾）**：公司采用模型强化加机理融合方式——监督学习动作空间大、数据分布远不足以支撑高维动作；强化学习强依赖仿真环境，纯强化学习难以做到sim-to-real迁移；需将强化学习决策空间与任务设定（state-action对）做很好限定，上层用强化学习做决策，底层用MPC、DWA等传统方法执行，实际部署中能提升整体性能。
+- **发言者9**：认为复杂任务应先模仿后强化——从历史看AlphaStar、GPT等复杂问题都是先模仿后强化；from scratch跑强化学习样本复杂度不可接受，人类模仿提供的先验信息没有坏处；单独模仿不行（人类行为不一定最优，需强化达到superhuman），单独强化也不行（除非任务足够简单）。
+- **发言者5**：PID能做的系统必有反馈，反馈可作为强化学习的reward——过去用PID效果不够好，现在通过强化做得更好，但PID能做说明反馈存在，强化必然走得成。
+- **发言者11**：认为模仿学习与强化学习并不冲突——只是获取运动先验的不同方式，有现成数据可从模仿学习角度做，没有数据可用DeepMind的Motion Matching等强化学习方式先获取，再通过BC形式建模latent，之后用RL快速找到对应latent完成任务。
+## 数据采集与仿真
+- **发言者11**：强调数据采集时视角控制和标定非常重要——Open X等数据集融合多家数据、相机视角无法固定，视角非常影响policy表现；Open X等数据集只捕捉本体信息（末端、关节角度、力矩），缺少物体运动信息，其采集时一定要记录物体运动，当时设备有限只能采集刚体和关节体。
+- **发言者4（博士生，all in真实数据采集路线）**：仿真技术对柔性物体模拟不足——叠衣服、系鞋带等任务需要IPC等先进图形学技术，算力要求高且掌握者少（如UCLA蒋正凡夫）；真实数据采集是低成本方案，"真实世界就是最好的仿真器"；终极数据采集形态是脑机接口或可穿戴设备，能无感采集多模态数据；互联网视频数据与机器人所需数据差异大——网上教叠衣服的视频都是平铺状态，但机器人见到的是从洗衣机拿出揉成一团的状态，人类习以为常的简单事恰恰是机器人最缺的数据。
+- **发言者2（主持人）**：仿真数据与少量真机数据结合可显著提升成功率——300条仿真数据加20条真机数据，用简单的pretrain+微调方法即有显著提升；仿真数据可覆盖物体随机位置、随机orientation、任意初始状态；互联网数据质量低，如ego4d数据集清洗耗时三个月。
+- **发言者7**：真实数据还是仿真数据应case by case看成本——室内服务机器人真机数据收集有可行性，自动驾驶corner case收集危险；提出2025年应推广利用无标注真实数据（如segment anything、depth anything），不要再讨论真实与仿真数据比例（1:9、2:8、5:5等观点）。
+- **发言者7（回应国产仿真系统问题）**：有公司（如宋应）赌卡脖子风险做国产替代，这是business层面的复杂问题，技术上最终会比较统一。
 # 达成共识与解决方案
-**未形成统一结论**。本场研讨围绕具身智能的硬件形态、世界模型、策略学习路线与数据来源四个议题展开，各方观点存在明显分歧，未达成一致意见。但讨论中形成了若干倾向性认识与主流意见，具体如下：
-## 硬件形态与模型架构
-- **软硬件协同优化**：发言者2提出具身智能是软硬件协同优化的范式，以松灵产品两代迭代为例，第二代在遥操与策略部署上优于第一代；夹爪加凝胶后可反馈触觉、增加摩擦力，说明硬件改进能提升算法性能。
-- **模型分层而非统一**：发言者5主张大模型不应从上到下完全统一，至少应分大脑与小脑两层——大脑保持稳定，小脑需适应肢体变化（以手断后大脑仍能工作、小脑需适应新构型为例）；发言者6认为当前多模态大模型微调方案不是终极形态，世界模型可能更接近人脑水平，但人形与特种机器人将并存。
-- **硬件可靠性要求**：发言者4提出具身智能实验用硬件需高寿命、高可靠性，现有工业机械臂易因模型预测失误撞坏，难以支撑大规模真机评估，需个人柔顺硬件结构支持scale up。
+**未形成统一结论**。本场围绕具身智能大模型与硬件形态、世界模型、强化学习与模仿学习路线、数据采集与仿真四个议题展开研讨，各方观点存在明显分歧，但形成了若干倾向性认识与主流意见。
+## 具身智能大模型与硬件形态
+- **大模型分层架构**：发言者5认为大模型不应从上到下统一为一个模型，至少应分两层——大脑不变、小脑适应肢体；其依据是若硬件（如软体机器人）变化，统一模型需完全重新训练，而分层架构下大脑可保持稳定，仅小脑适配新的动力学。发言者6认为当前多模态大模型微调方案不是终极方案，世界模型可能更接近人脑水平，但最终形态仍难预测。
+- **机器人形态收敛**：发言者6认为人形机器人与特种机器人将并存——人形机器人因现实环境为人设计而存在，特种机器人已在工业生产中大量应用（如车厂、微电子制造厂机械臂实现97%以上自动化）。发言者3提出形态收敛问题（人形或可变形的非人形），未获统一回应。
+- **融资规模预测**：发言者7预测具身智能融资将经历四波，分别达到自动驾驶、大模型、互联网的规模；当前10亿人民币规模很小，未来3–4波技术变革将深刻改变本体形态与大模型形态。
 ## 世界模型
-- **两领域定义差异**：发言者8指出强化学习领域世界模型概念源于1990年Dyna-Q，核心是可交互性（输入观测与动作、输出下一时刻观测）；发言者7认为CV界世界模型追求动态重建物理世界，可作为RL世界模型的工具，但当前技术不成熟，且RL与CV关注点不同——RL更端到端，CV更关注解耦表征。
-- **数据规模与归纳偏置权衡**：发言者7提出数据规模与归纳偏置存在权衡——数据充足时归纳偏置需求减少，数据稀缺时需要更多归纳偏置；以ImageNet、GPT成功说明大规模学习可减少归纳偏置，而UniSim等新模型仍需三维归纳偏置。
-- **世界模型统一性存疑**：发言者5认为世界模型可能无法统一，因存在歧义问题（游戏与物理世界观测相同但动力学不同）；发言者9认为强化学习的世界模型是任务导向的，CV世界模型并非必要，但不同物理结构可共享统一表征。
-## 策略学习路线
-- **混合路线倾向**：发言者10表示公司采用模型强化加机理融合方式，因监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且难以迁移；发言者9认为复杂任务应先模仿后强化，单独模仿无法超越专家水平，单独强化样本复杂度不可接受，但工程手段可解决先模仿后强化可能带来的问题。
-- **反馈作为奖励信号**：发言者5提出PID控制必有反馈，可将其作为强化学习在执行过程中的奖励信号，这是真机强化学习reward获取的可行路径。
-- **模仿与强化不冲突**：发言者11认为两者并非本质冲突，可先通过模仿学习或强化学习获取运动先验（latent），再通过强化学习完成任务。
+- **强化学习视角**：发言者8认为世界模型第一要义是可交互（源于1990年Dyna-Q），其次需体现物理规律，最后引入3D等模态信息；当前世界模型在物理规律体现上欠缺明显。发言者9认为强化学习的世界模型是任务导向的，只需支持策略学习即可，不一定需要CV式的完整世界模型。
+- **计算机视觉视角**：发言者7认为CV领域世界模型追求动态重建物理世界，可作为RL中世界模型的工具，但当前技术不成熟；三维表征技术栈深，RL研究者难以在博士阶段完全掌握，导致RL领域不关注三维表征。
+- **世界模型统一性**：发言者5认为世界模型可能无法统一——同一观测（如游戏与真实世界跳楼）对应不同动力学，存在歧义问题；但策略（policy）可以统一，因人类同一大脑可适应不同物理环境。发言者9提出反例：可在世界模型中加condition区分不同物理结构，但发言者5认为M个独立模型比一个高维可控模型更易实现。
+- **Inductive bias**：发言者7提出数据规模决定是否需要inductive bias——数据多则不需要，数据少则需要；当前在NeRF等任务上需要3D inductive bias，未来数据规模化后可能不再需要。
+## 强化学习与模仿学习
+- **业界实践**：发言者10表示公司采用模型强化加机理融合方式——监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且sim-to-real迁移不佳；实际做法是限制强化学习的决策空间与任务设定，上层用强化学习做决策，底层用MPC等传统方法执行。
+- **先模仿后强化**：发言者9认为复杂任务应先模仿后强化——从零强化学习样本复杂度不可接受，模仿提供先验信息；单独模仿无法超越专家水平，单独强化仅适用于简单任务；AlphaStar、GPT等复杂系统均采用此路线。
+- **反馈作为reward**：发言者5认为PID能做的系统必有反馈，该反馈可直接作为强化学习的reward——这是其拔插任务中真机强化学习reward获取的关键依据。
+- **模仿与强化不冲突**：发言者11认为两者只是获取运动先验的不同方式——有数据可用模仿学习，无数据（如人类复杂运动）可用强化学习生成，最终都建模为latent状态供任务使用。
 ## 数据采集与仿真
-- **仿真数据加少量真机数据**：发言者2提出仿真数据可弥补真机数据不足——300条仿真数据训出的策略直接部署真机成功率很低，但加上20条左右真机数据后成功率显著提升；仿真数据可覆盖物体随机位置、朝向与初始状态。
-- **数据质量关键要素**：发言者11强调数据采集时视角控制与标定至关重要（手眼标定至今仍有文章在解决），且必须记录物体运动而不仅是本体信息；发言者2指出互联网数据质量低，ego4d数据集清洗耗时三个月。
-- **真实数据规模化路径**：发言者4认为真实数据是低成本方案（相比高性能仿真算力），但现有采集方式难以达到GPT-3级别数据量；提出终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备是可行方案；互联网视频数据与机器人所需数据差异大（如叠衣服场景，网上视频多为平整状态教学，机器人需处理从洗衣机取出揉成一团的初始状态）。
-- **无标注数据利用**：发言者7提出2025年应大规模利用无标注真实数据（如segment anything、depth anything），不再局限于讨论有标注真实数据与仿真数据的配比。
+- **数据质量**：发言者11强调视角控制与标定至关重要——Open X等数据集相机视角不固定，影响policy表现；其OpenLink数据集记录物体运动（刚体与关节体），弥补现有数据集只含本体信息的不足。
+- **真实数据采集**：发言者4主张真实数据是低成本方案——柔性物体仿真需IPC等先进技术，算力要求高且掌握者少；真实世界本身就是最好的仿真器。终极采集形态是脑机接口或可穿戴设备，实现无感多模态采集；互联网视频数据与机器人所需数据差异大（如叠衣服视频均为平铺状态，缺少从混乱状态展平的记录）。
+- **仿真与真实数据结合**：发言者2报告实验结果——300条仿真数据训出的策略直接部署真机成功率很低，但加上20条真机数据后成功率显著提升；仿真数据可提供海量随机初始状态，真机数据弥补sim-to-real gap。
+- **无标注数据**：发言者7提出2025年应推广利用无标注真实数据（如segment anything、depth anything模式），不再局限于讨论有标注真实数据与仿真数据的比例。
+- **国产仿真系统**：发言者7回应国产仿真系统问题——有公司（如宋应）赌卡脖子风险做国产替代，business层面复杂，技术上最终会统一；发言者2指出Isaac Lab等英伟达生态目前支持柔性物体仿真接口，但中国是否强依赖英伟达生态未定。
 # 未决分歧与后续探索
-## 硬件形态与模型架构
-- **具身智能硬件形态收敛方向**：发言者3提出疑问，具身智能身体最终收敛为人形机器人还是科幻片中可变形形态；发言者6认为人形机器人与特种机器人将并存——人形因现实环境为人设计而存在，特种机器人在车厂、微电子制造厂等场景已实现97%以上自动化；发言者7从产业角度预测，未来三至四波技术变革将深刻改变具身大模型的硬件与云端模型形态，具体形态暂时无法预测。
-- **大模型是否应从上到下统一**：发言者5主张不应是单一模型贯通最上至最下，至少应分大脑与小脑两层——以手断后大脑仍能工作、小脑需适应肢体变化为例，认为小脑应adaptive到肢体，而非更换大脑；发言者6认为当前多模态大模型微调方案不是终极方案，世界模型可能更接近人类水平，但人脑新架构出现前难以预测最终形态。
-- **硬件可靠性需求**：发言者4提出具身智能实验需要硬件高寿命与高可靠性，现有工业机械臂并非为大规模真机评估设计，撞几次即损坏，难以可靠scale up，需要个人柔顺的硬件结构支撑规模化评估；发言者2认为具身智能是软硬件协同优化范式，以松灵两代产品对比说明硬件迭代提升遥操与策略部署效果，凝胶夹爪可反馈触觉且抓取更稳。
-## 世界模型定义与实现路径
-- **世界模型是否需要三维归纳偏置**：发言者7认为CV界世界模型追求重建物理世界，可作为RL世界模型的工具，但当前技术不成熟；三维表征技术栈深，RL博士生难以完全学习，导致RL领域不关注三维表征；发言者7提出数据规模与归纳偏置的权衡——数据多时归纳偏置需求减少，数据少时需求更多，并称梦想写一篇题为data bias trade off的论文；发言者8从强化学习角度指出世界模型第一要义是可交互，源于1990年Dyna-Q，当前世界模型在物理规律体现上欠缺明显。
-- **世界模型能否统一**：发言者5认为世界模型可能无法统一——以游戏主角跳楼与物理世界跳楼结局不同为例，相同观测对应不同dynamics，存在完全歧义问题，M个独立世界模型比一个高维可控condition模型更可实现；发言者9提出反例，认为不同物理结构可有相同统一表征，policy能识别condition，世界模型为何不能；发言者5回应称加condition后工程难度高，用GPT模型回归atari games大概率是强记；发言者9认为强化学习的世界模型是任务导向的，CV世界模型并非必要，只要有助于学策略即可。
+## 具身智能形态
+- **人形 vs 特种机器人**：发言者6认为人形机器人与特种机器人将并存——现实中桌椅等设施为人设计，人形机器人（双足或轮式、带灵巧手）会占很大比例；特种机器人已在车厂、微电子制造厂实现97%以上自动化，同样大量存在。发言者3提出形态收敛问题（人形还是科幻片中可变形的方块），未获直接回应，形态比例与主导形态未定论。
+- **大模型是否应贯通硬件层**：发言者5主张大模型不应从上到下贯通为一个模型，至少应分两层——大脑不变、小脑自适应肢体；理由是若新硬件（如软体机器人）出现，贯通式大模型需完全重新训练。发言者6认为当前基于多模态大模型微调的大脑方案不会是终极形态，世界模型可能更接近人脑水平，但可能也不是最终形态。发言者7从产业角度预测未来3–4波技术变革将深刻改变具身大模型硬件与云端模型形态，具体形态暂时无法预测。
+## 世界模型
+- **世界模型是否需要三维表征**：发言者8（强化学习视角）认为世界模型第一要义是可交互（可据此学策略），其次需体现物理规律，最后才引入3D等信息；发言者7（CV视角）认为CV界追求重建物理世界，可作为RL世界模型的工具，但当前技术不成熟，RL领域博士生难以完整学习三维视觉技术栈，导致RL界不太关注三维表征。发言者9认为强化学习的世界模型是任务导向的，只要有助于学策略即可，不一定需要CV式世界模型。
+- **世界模型能否统一**：发言者5认为世界模型可能无法统一——同一观测可能对应不同物理dynamics（如游戏与现实中从楼上跳下结局不同），存在歧义问题；但策略（policy）可能统一，因为同一大脑可同时适应游戏与现实。发言者9提出反例：可在世界模型中加condition（区分游戏或现实）实现统一，但发言者5认为这需极高维的controllable condition，工程上M个独立模型更简单，且目前没有单一世界模型能建模所有Atari游戏。发言者9进一步追问策略是否也需分成N个，发言者5回应策略可通过更长的observation窗口隐式体现condition，无需显式加入。
+- **是否需要inductive bias**：发言者7提出数据规模决定是否需要inductive bias——数据多时所需bias少，数据少时所需bias多；当前在NeurIPS上刷点需要3D inductive bias，但工业界数据scaling up后可能不需要，更端到端方式会更好。发言者9对此提出异议，认为不能简单以是否带inductive bias区分RL与CV世界模型的优劣。
 ## 强化学习与模仿学习路线
-- **最终策略学习路线**：发言者10表示公司采用模型强化加机理融合方式，因监督学习数据分布远不足以覆盖高维动作空间，纯强化学习强依赖仿真环境、sim-to-real迁移困难，需将强化学习决策空间与任务设定限制好，上层用强化学习做决策、底层用MPC或DWA等传统方法执行；发言者9认为复杂任务应先模仿后强化，单独模仿无法达到专家水平（除非任务即专家行为），单独强化样本复杂度不可接受，先模仿再强化不会导致强化效果变差，工程手段可解决；发言者11认为模仿学习与强化学习并无本质冲突，运动先验有数据可用模仿学习获取，无数据可用强化学习生成，再通过强化学习完成任务。
-- **真机强化学习的奖励获取**：发言者2提出真机复杂任务中reward如何获取的问题，仿真中有上帝视角，真机上detection与传感器有偏差；发言者5回应称PID控制必有反馈，所有PID能做的系统必然有反馈，可完全拿该反馈作为强化学习的reward，过去PID效果不够好，现在通过强化可做得更好。
+- **最终路线是融合还是单独使用**：发言者10（业界）表示公司采用模型强化加机理融合方式——监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境、sim-to-real迁移困难；需将强化学习的决策空间与任务设定做良好限定（如任务分层，上层强化学习做决策，底层用MPC等传统方法执行）。发言者9认为复杂任务应先模仿后强化——单独模仿无法超越专家（除非任务就是复现专家行为），单独强化from scratch样本复杂度不可接受；先模仿提供先验信息不会损害强化效果，工程手段可解决学术论文宣称的负面问题。发言者11认为模仿学习与强化学习并无本质冲突——运动先验有现成数据可用模仿学习获取，没有数据可用强化学习（如DeepMind的mimic）生成，再以BC形式建模latent，任务层用RL快速找到对应latent。
+- **真机强化学习的reward获取**：发言者2提出真机场景下复杂任务reward难以获取（仿真有上帝视角，真机检测与传感器有偏差）。发言者5回应：PID能做的系统必然有反馈，该反馈可直接作为强化学习的reward——过去用PID效果不够好，现在用强化可做得更好；只要PID能做，强化必然走得成。
 ## 数据采集与仿真
-- **真实数据与仿真数据比例**：发言者7认为应case by case看成本，室内服务机器人真机数据收集有可行性，自动驾驶corner case收集危险；发言者7提出2025年应迈向大规模利用无标注真实数据，如segment anything、depth anything，不再讨论真实与仿真有标注数据的比例问题。
-- **数据采集规模化方案**：发言者4主张真实数据是低成本方案，现实生活是最好的仿真器，但现有采集方式即使多一两个数量级也难以达到GPT-2、GPT-3级别数据量，终极形态可能是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备在人们做事过程中采集是较能scale的方案；发言者4指出互联网视频数据与机器人所需数据差异大——网上教叠衣服的视频是平铺状态，机器人需要的是从洗衣机取出揉成一团再展平的数据，常见易完成的事情恰是机器人最缺的数据。
-- **数据质量与视角控制**：发言者11强调采集数据时视角控制与标定非常重要，open X等数据集相机视角无法固定、影响policy表现，且只捕捉本体信息、缺少物体运动，orkin从采集角度出发必须记录物体运动，设备有限时只能采集刚体和关节体。
-- **仿真数据与真机数据结合**：发言者2表示用仿真生成300条数据训完策略直接去真实世界测试成功率很低，但300条仿真数据加20条左右真机数据成功率显著提升，方法只是pretrain一个model再用真机数据微调；发言者2指出柔性物体仿真并非解决不了，而是图形学领域认为机器人布料模拟不够格发顶会、看不上这类研究，机器人领域又不懂相关计算，未来可能有发展。
-- **国产仿真系统能否替代英伟达生态**：发言者2提出中国是否强依赖英伟达生态的问题；发言者7回应称有朋友宋应赌会被卡脖子、在做国产替代，这是business层面的复杂问题，技术上最终会比较统一，但工作人员不会直接touch这个生意。</t>
+- **真实数据 vs 仿真数据比例**：发言者2认为仿真数据与少量真机数据结合可显著提升成功率——300条仿真数据加20条真机数据即可明显提升，但大量真机数据采集成本高（实习生熬夜做实验）。发言者7认为应case by case看成本——室内服务机器人真机数据可行，自动驾驶corner case采集危险；并主张2025年应加入第三个domain：无标注真实数据，像segment anything、depth anything那样大规模利用无标注数据，不再纠结真实与仿真数据比例（1:9、2:8、5:5等说法）。
+- **数据质量与采集方式**：发言者11强调视角控制与标定至关重要——Open X等数据集相机视角不固定，影响policy表现；其团队（orkin）采集时严格固定视角，并记录物体运动（刚体与关节体），而非仅记录本体信息。发言者4主张真实数据采集是低成本方案——柔性物体仿真需IPC等先进图形学技术，算力要求高且掌握者少（如UCLA蒋正凡夫），进展缓慢；终极采集形态是脑机接口或可穿戴设备，实现无感多模态采集；互联网视频数据与机器人所需数据差异大（如叠衣服视频都是平铺状态，没有从洗衣机取出揉成一团的状态），需补上这一环节。
+- **仿真系统国产化**：发言者2提出中国是否强依赖英伟达生态（Isaac Sim/Isaac Lab目前支持柔性物体仿真接口，比其他架构好用）。发言者7回应：有公司（如宋应）赌卡脖子风险做国产替代，这是business层面的复杂问题；技术上最终会较统一，标准化后应无大问题。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>79.5</v>
+        <v>72.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/7867</t>
+          <t>21458/7665</t>
         </is>
       </c>
     </row>
@@ -2991,59 +2973,55 @@
       <c r="C7" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审，由最高人民法院公开开庭审理，审判长李少平，合议庭成员魏文超、黄年、王海峰、葛洪涛，法官助理张瑞。庭审围绕三个争议焦点进行审理：国开行抵押权是否构成善意取得、罚息复利计算及起算日期、东源煤电与东源煤业是否应连带给付违约金。各方充分发表辩论意见后，合议庭休庭评议并提出调解方案，各方均无异议，自愿达成调解协议，法院予以确认并出具调解书。
+本案为上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷案二审开庭，由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，公开开庭审理。各方当事人对出庭人员身份均无异议，并确认已收到诉讼文书及开庭传票。庭审围绕三个争议焦点展开法庭调查与辩论：国开行是否尽到审查义务并构成善意取得抵押权；一审判决对罚息、复息的计算及起算日期是否认定错误；东源煤电、东源煤业是否应当连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人均无异议，自愿达成调解协议，法院予以确认并出具调解书。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国开行） | 请求撤销一审判决，改判支持其抵押权、罚息复利及违约金主张 | 主张抵押设备为通用设备，无唯一标识码，已对抵押人曲靖电力公司进行融资租赁登记查询且无结果，构成善意取得；利息计算至2017年12月20日，罚息自2018年6月13日发函要求还款之日起算，复利按合同第6条第4款约定计算；依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金，且东源煤电未配合办理账户管理及柜台前移手续。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 主张2015年12月2日邮件附件《东源公司融资情况统计表》已用红色标注抵押设备与招银租赁设备名称相同，国开行未尽注意义务；合同约定应限期偿还而非立即偿还，国开行未给予合理期限；罚息不应作为复利计算基数；国开行未举证证明违约行为，且未按合同约定先行限期纠正，无权主张违约金。 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 主张国开行提供的是2018年9月查询证书而非2015年12月抵押时点查询结果，不符合人行规定；国开行审查义务应扩展至东源煤电；东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权；国开行未在抵押时点查询登记系统，不构成善意取得。 |
+| 上诉人（国开行） | 请求撤销一审判决，改判支持其利息、罚息、复利及违约金主张，确认其对案涉设备享有抵押权。 | 主张已按央行规定查询融资租赁登记系统，未发现登记，审查义务仅限于抵押人曲靖电力公司，设备为通用设备无唯一标识码，故构成善意取得；利息、罚息、复利计算有合同依据，东源煤电未配合办理账户管理及柜台前移手续构成违约，应支付千分之一违约金。 |
+| 被上诉人（东源煤电） | 请求驳回上诉，维持一审判决。 | 主张国开行收到2015年12月2日邮件（抵押设备名称以红色标注且与招银租赁设备名称完全一致）后应尽注意义务进行核查；宣布贷款提前到期应限期偿还而非立即偿还；罚息不应作为复利计算基数；国开行未举证证明违约行为，且未按合同约定先限期纠正。 |
+| 被上诉人（东源煤业） | 请求驳回上诉，维持一审判决。 | 主张国开行未举证证明东源煤业存在违约行为，且未按合同约定先发出限期纠正的书面函件，故违约金请求不能成立。 |
+| 被上诉人（东源曲靖电力） | 请求驳回上诉，维持一审判决。 | 主张国开行未在抵押时点进行融资租赁登记查询，不构成善意取得；东源煤电出资行为属无权处分，电力公司未取得设备所有权。 |
+| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决。 | 主张国开行应提供2015年12月抵押时点的人行征信中心查询结果而非2018年9月的查询证书；东源煤电出资行为属无权处分；国开行未在抵押时点审查，不构成善意取得；罚息不应作为复利计算基数。 |
 # 举证与法庭调查
 ## 举证与质证
-- **国开行提交**：2018年9月对曲靖电力公司的融资租赁查询证书，证明其已尽查询义务；东源方质证认为该证书不符合要求，根据2014年93号中国人民银行规定，国开行应在抵押时点（2015年12月）进行查询。
-- **国开行提交**：证据54页、58页东源煤电公司、曲靖电力公司对设备的权属证明材料和股东会决议，证明抵押设备所有权属曲靖电力公司；招银租赁未对该组证据提出实质性质证意见。
-- **国开行提交**：证据108页融资租赁登记核查表，证明其已对曲靖电力公司名下融资租赁登记进行核查；招银租赁质证认为核查范围应扩展至东源煤电。
-- **招银租赁提交**：一审证据第7页回租设备清单，载明设备名称、生产厂家，但未载明型号；国开行质证认为该清单无法证明设备唯一性，且清单记载出厂日期为2012年3月1日，与国开行现场调查核实的铭牌生产日期（2013年11月、12月、2014年3月）不符。
-- **招银租赁提交**：2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元已实缴；国开行质证认为该报告已载明设备出资事项，招银租赁应当知道设备出资情况。
-- **东源方提交**：2015年12月2日邮件及附件《东源公司融资情况统计表》，证明已告知国开行抵押设备存在融资租赁情况；国开行质证认为该邮件系贷后审查材料，统计表中招银租赁栏记载抵押类型为不动产抵押，与本案融资租赁是两个法律概念，不能证明已履行告知义务。
-## 证人/鉴定陈述
-未提及
+- **东源煤电提交《东源公司融资情况统计表》**：主张2015年12月2日邮件已告知国开行招银租赁对恩洪电厂设备资产已办理抵押登记，且抵押设备名称以红色标注；国开行质证认为该邮件系贷后审查材料，其中招银租赁抵押类型为不动产抵押，与本案融资租赁系不同法律概念，不能证明已履行告知义务。
+- **国开行提交2018年9月融资租赁查询证书**：主张已按央行规定查询融资租赁登记系统，未发现曲靖电力公司设备有融资租赁登记；招银租赁质证认为该查询证书不符合要求，国开行应提供2015年12月抵押时点的人行征信中心查询结果。
+- **招银租赁提交回租设备清单**：主张案涉5套设备已登记，清单载明设备名称、数量、原值、净值、出厂时间、生产厂商及存放地点；国开行质证认为清单仅载明设备名称和生产厂家，未载明型号，且出厂日期为2012年3月1日，与国开行现场调查核实的铭牌生产日期（2013年11月、12月及2014年3月）不一致，不能证明系同一设备。
+- **招银租赁提交2013年、2015年审计报告**：主张报告已载明曲靖电力公司注册资本4亿元且已实缴，国开行应知悉设备出资情况；国开行质证认为设备未纳入资产负债表不等于企业不拥有资产，评估报告已确认资产存在。
+- **国开行提交证据54页、58页权属证明及股东会决议**：主张抵押设备所有权属曲靖电力公司，已尽审慎义务；招银租赁质证认为东源煤电出资行为属无权处分，电力公司未取得所有权。
+## 证人、鉴定与其他来源陈述
+- **审计报告**：招银租赁一审提交2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴，设备出资事项已载明。
+- **评估报告**：国开行主张在建工程价值5.7亿元，机器设备价值5.1亿元，报告确认上述资产存在，虽未纳入资产负债表但不影响所有权。
 ## 法官询问
-- **审判长询问**：各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果？国开行认为属行业强制规范，目的是防范金融风险；东源方认为属行业指导性规范，不当然产生物权后果；招银租赁认为非物权登记，但具有对抗效力。
-- **审判员询问**：央行融资租赁登记系统有几种查询方式？国开行称仅能通过查询单位名称查询；招银租赁称可通过公司名称或设备信息查询，但设备查询涉及种类物区分问题。
-- **审判员询问**：案涉5套设备登记时是否登记了唯一识别码？招银租赁称设备无唯一识别码，未登记；东源方补充称初始登记时将租赁物清单作为附件上传，清单载明设备名称、数量、原值、净值、出厂时间、生产厂商及存放地点。
-- **审判员询问**：国开行贷款前风控资料中是否有内部规定要求必须查询融资租赁登记，未查到也需保留记录？国开行称无此规定，因未查询到结果故未保留记录。
-- **审判员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁称非必填项，案涉设备无唯一识别码。
-- **审判员询问**：设备安装后发电机上是否有唯一标识码？招银租赁称铭牌上仅有型号和参数，同型号设备铭牌相同。
-- **审判员询问**：违反查询规范在多大程度上导致融资租赁司法解释第9条第2款法律后果，是基本查询义务还是全面审慎义务？国开行认为系基本义务，仅需对抵押人查询；招银租赁认为系严格义务，未查询即不构成善意。
-- **审判员询问**：若银行通过其他途径知晓动产属融资租赁物，是否无需查询？国开行认为基本义务仍需履行；东源方认为仍需查询以确认权属；招银租赁认为必须通过央行系统查询，因其他方式无法证明。
-- **审判员询问**：融资租赁司法解释第9条第2款举证责任如何分担？国开行认为按谁主张谁举证原则；招银租赁认为第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
-- **审判长询问**：对因不同登记机构产生的登记信息冲突有何意见和建议？国开行认为系系统性问题，建议整合信息；东源方称非专业机构，无成熟建议；招银租赁建议从立法、行业协会、技术操作三层面改进。
+- **审判长询问**：生产设备作为动产，各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果？国开行认为属行业强制性规范，旨在防范金融风险；东源方认为属行业指导性规范，不产生物权后果；招银租赁认为属行业性强制性规范，可产生对抗效力，但不影响物权法定效果。
+- **合议庭成员询问**：央行融资租赁登记系统有几种查询方式？国开行称仅能通过查询单位查询；招银租赁称可通过公司名称或设备信息两种方式查询，但设备查询需设备特定化。
+- **合议庭成员询问**：案涉5套设备登记时是否登记唯一识别码？招银租赁称设备无唯一识别码，故未登记；合议庭成员追问设备安装后发电机上是否有唯一标识码，招银租赁称铭牌上仅有型号和参数，无唯一识别码。
+- **合议庭成员询问**：国开行贷款前审查时，内部是否有规定必须查询融资租赁登记系统，未查到也需保留查询记录作为风控材料？国开行称按央行规定查询，因未查到记录故未保留。
+- **合议庭成员询问**：国开行认为查询义务是基本义务还是全面审慎义务？国开行认为系基本义务，审查对象限于抵押人曲靖电力公司；招银租赁认为系严格义务，银行未查询即不构成善意。
+- **合议庭成员询问**：若银行通过其他途径知晓抵押物属融资租赁物，是否仍需查询登记系统？国开行认为基本义务必须履行；东源方认为仍需查询以确认权属；招银租赁认为必须通过央行系统查询，因其他方式无法证明。
+- **合议庭成员询问**：融资租赁司法解释第9条第2款举证责任如何分担？国开行认为按谁主张谁举证原则；招银租赁认为第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
+- **审判长询问**：因不同登记机构产生的登记信息冲突，各方有何意见和建议？国开行认为系系统信息不完整、条块分割所致，建议整合；东源方认为系统整合有必要但提不出成熟建议；招银租赁建议从立法、行业协会、操作技术层面改进。
 ## 争议焦点与辩论
-### 争议焦点一：国开行抵押权是否构成善意取得
-- **国开行主张**：抵押设备为通用设备，无唯一标识码，无法通过设备查询融资租赁登记；其已对抵押人曲靖电力公司进行查询且无结果，尽到审慎义务，构成善意取得。
-- **东源方主张**：2015年12月2日邮件附件《东源公司融资情况统计表》已用红色标注抵押设备与招银租赁设备名称相同，国开行作为专业金融机构应尽注意义务，进行适当核查。
-- **招银租赁主张**：国开行提供的是2018年9月查询证书，而非2015年12月抵押时点查询结果，不符合人行规定；国开行审查义务应扩展至东源煤电，因其系借款人及抵押人全资控股母公司。
-- **东源方补充**：东源煤电出资行为系无权处分，因招银租赁2012年已取得设备所有权；设备交付到货即取得所有权，招银租赁在交付时点已获所有权。
-- **国开行反驳**：融资租赁登记系行业规范，非物权登记；其审查义务仅限于抵押人曲靖电力公司，不能任意扩大至关联企业。
-### 争议焦点二：罚息复息计算及起算日期
-- **国开行主张**：利息计算期间为2017年12月21日至2018年6月12日，利息合计21,795,727.68元；罚息自2018年6月13日起算至2019年2月19日，罚息41,050,579.57元；复利自2018年3月21日起算至2019年2月19日，复利1,918,206.23元。
-- **东源方主张**：合同约定应限期偿还而非立即偿还，国开行未给予合理期限；罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条及最高院判例；复利再计算复利无合同依据。
-- **国开行反驳**：东源煤电已严重违约且无履约能力，讨论合理期限无意义；合同第6条第4款明确约定对逾期借款利息按罚息利率计收复利，且东源煤电未上诉，一审已支持罚息复利。
-- **东源方再反驳**：合同条款存在歧义，应作不利于格式合同提供方（国开行）的解释。
-### 争议焦点三：东源煤电、东源煤业是否应连带给付违约金
-- **国开行主张**：依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续。
-- **东源方主张**：国开行未举证证明东源煤电存在违约行为，举证不能后果应由其承担；国开行未按合同约定先行发出限期纠正函，无权直接主张违约金。
+- **争议焦点一：国开行是否尽到审查义务，是否构成善意取得抵押权**
+  - **国开行主张**：审查义务仅限于抵押人曲靖电力公司，已按央行规定查询融资租赁登记系统且未发现登记，设备为通用设备无唯一标识码，无法通过设备查询，故构成善意取得。
+  - **东源方主张**：国开行作为专业金融机构，收到2015年12月2日邮件（抵押设备名称以红色标注且与招银租赁设备名称完全一致）后应尽注意义务进行核查，避免重复抵押。
+  - **招银租赁主张**：国开行应提供2015年12月抵押时点的人行征信中心查询结果而非2018年9月的查询证书；东源煤电出资行为属无权处分，电力公司未取得所有权；国开行未在抵押时点审查，不构成善意。
+- **争议焦点二：一审判决对罚息、复息的计算及起算日期是否认定错误**
+  - **国开行主张**：利息自2017年12月21日计算至2018年6月12日合计21,795,727.68元，罚息自2018年6月13日计算至2019年2月19日合计41,050,579.57元，复利自2018年3月21日计算至2019年2月19日合计1,918,206.23元。
+  - **东源方主张**：借款合同第24条第2款第2项约定宣布提前到期应限期偿还而非立即偿还；根据《人民币利率管理规定》第21条及合同第6条第4款，罚息不应作为复利计算基数；复利再计算复利无合同依据。
+- **争议焦点三：东源煤电、东源煤业是否应当连带给付违约金**
+  - **国开行主张**：依据合同第24条第3项，东源煤电未按第13条、第14条配合办理账户管理及柜台前移手续，应支付千分之一违约金。
+  - **东源方主张**：国开行未举证证明东源煤电存在违约行为，且未按合同约定先发出限期纠正的书面函件，故违约金请求不能成立。
 # 庭审结果
-本案经调解结案，各方自愿达成调解协议，法院予以确认并出具调解书。调解方案主要内容：①国开行对东源煤电的债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元；②招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；③国开行对93项设备有抵押权，招银租赁对6项设备有所有权，双方对案涉全部发电设备整体盘活处置，变现款各得50%；④调解书生效后20日内，国开行向一审法院申请执行，启动司法处置程序；⑤若司法变现不能，国开行和招银租赁放弃对案涉设备权益，由东源曲靖电力自主生产经营；⑥东源曲靖电力承担案涉设备管理费用并无条件配合司法处置；⑦一审判决第2项、第4项无争议，按判项内容确认；⑧二审诉讼费用由国开行和东源煤电各承担50%。</t>
+本案三个争议焦点为：国开行是否尽到审查义务并构成善意取得抵押权；一审判决对罚息、复息的计算及起算日期是否认定错误；东源煤电、东源煤业是否应当连带给付违约金。经合议庭休庭评议，各方当事人自愿达成调解协议，法院予以确认并出具调解书。调解方案主要内容：国开行对东源煤电的债权扣除破产中已清偿本金外，利息、罚息、复利合计6474.4513万元；招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权，招银租赁对6项设备有所有权，双方对案涉全部发电设备整体盘活处置，变现价款各得50%；调解书生效后20日内由国开行向一审法院提出执行申请；若司法变现不能，双方放弃对案涉设备权益，由东源曲靖电力自主生产经营。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>86.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/3726</t>
+          <t>28485/3690</t>
         </is>
       </c>
     </row>
@@ -3200,43 +3178,55 @@
       <c r="C8" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持并汇报。验收组于18、19号提前介入，20号召开首次会议，对卢萨卡、蒙泽两点开展内业与外业检查。卢萨卡点已完成除带料调试以外的所有验收工作，蒙泽点利用现场资源顺带完成全部验收（含带料调试），姆皮卡点现场验收尚未开展，其内业资料已提前送至卢萨卡。内业检查分管理组和技术组，按合同及规范执行，项目执行团队人员基本在岗，内业资料基本满足标准要求，但分类整理和签字规范性需完善；竣工文件基本达到组卷成册要求，但资料分散，需汇总至卢萨卡。外业检查分建筑、安装、设备三部分：建筑部分原材料集中采购、质量良好，但局部有损伤和排水需检查；安装部分钢结构合格，但监控管线接头有脱落；设备部分运行正常，产能符合设计指标；蒙泽厂区混凝土路面有少量开裂。财务检查符合规范，中基公司无挪用资金情况。验收组提出整改要求，管理组田组长和技术组龚总承诺会后落实，合作局领导金昌柱要求出报告前完成整改并复核。项目有动用不可预见费情况，需完善证据资料，后续专项对接。
+本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持，合作局领导金昌柱、公司国内领导林总及管理组、技术组参会。验收组于18、19号提前介入项目摸排，20号召开首次会议，目前已完成卢萨卡点除弹料加工调试以外的全部验收工作，蒙泽点已完成全部验收并顺带进行带料调试和试生产，某皮卡点现场验收尚未开展，内业资料已提前拿到卢萨卡。内业检查分管理组和技术组，项目执行团队编制了施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足标准要求，竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需完善。外业检查覆盖建筑、安装、设备三个板块，建筑部分主材从国内采购或从卢萨卡集中采购，钢结构材料从国内定制，设备参照中国标准定制，蒙泽点工艺设备运行正常，产能符合设计指标。验收组提出人员履约、内业资料、现场整改等整改项，管理组和技术组承诺会后细化问题并制定方案整改。财务检查符合规范，不可预见费使用需完善依据证据。合作局领导要求重视蒙泽厂区混凝土路面开裂问题，分析原因并制定整改方案，所有问题在出报告前完成整改并形成闭环；公司领导要求按标准完成验收并注意交通安全和疫情防控。
 # 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 已完成除带料调试以外的所有验收工作 | ✅已完成 |
-| 蒙泽点验收 | 利用现场资源顺带完成全部验收，含带料调试，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
-| 姆皮卡点验收 | 现场验收尚未开展，内业资料已提前送至卢萨卡 | ⏸未开始 |
-| 内业资料 | 基本满足标准要求，但分类整理和签字规范性需完善；竣工文件基本达到组卷成册要求，但资料分散，需汇总至卢萨卡 | 🔄进行中 |
-| 外业检查-建筑 | 原材料集中采购、质量良好，但局部有损伤和排水需检查 | 🔄进行中 |
-| 外业检查-安装 | 钢结构安装合格，但监控管线接头有脱落 | 🔄进行中 |
-| 外业检查-设备 | 设备运行正常，工艺流程满足生产要求，产能符合设计指标 | ✅已完成 |
-| 财务检查 | 账户设置、资金往来、银行开户等符合规范，中基公司无挪用资金情况 | ✅已完成 |
+| 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作 | ✅已完成 |
+| 蒙泽点验收 | 已完成全部验收工作，并顺带进行带料调试和试生产，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
+| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡 | ⏸未开始 |
+| 内业检查 | 管理组和技术组按合同组建执行团队，编制施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足标准要求，竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需完善 | 🔄进行中 |
+| 外业检查-建筑 | 主材从国内采购或从卢萨卡集中采购，内在品质和外观通过查验资料和现场抽检达到良好标准，存在局部损伤、排水、混凝土路面开裂等问题待整改 | 🔄进行中 |
+| 外业检查-安装 | 钢结构材料从国内定制，施工工艺和外观质量满足规范标准，存在监控管线接头脱落、提升桶位置雨水倒灌风险、廊桥横向支撑不足等问题待整改 | 🔄进行中 |
+| 外业检查-设备 | 设备参照中国标准定制，厂家高峰期派十几名人员现场指导安装，蒙泽点工艺设备运行正常，产能符合设计指标 | ✅已完成 |
+| 财务检查 | 财务账户设置、资金往来、银行开户等符合财务处理规范和标准 | ✅已完成 |
+| 不可预见费使用 | 有动用不可预见费的情况，需完善依据证据和数据 | 🔄进行中 |
 # 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 蒙泽厂区混凝土路面开裂 | 中 | 可能影响项目移交后使用，存在大面积开裂隐患 | 管理组、总包单位 | 分析开裂原因，制定科学合理的整改方案，出报告前完成整改并复核 |
-| 监控管线接头脱落 | 中 | 可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
-| 卢萨卡点提升桶位置雨水倒灌 | 中 | 雨水可能倒灌，影响设备运行 | 施工组 | 检查并考虑增加覆盖面积或采取技术措施解决 |
-| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照及证件有效期需完善，影响验收报告闭合 | 管理组、技术组 | 完善人员统计和护照证书收集，与国内人力资源对接 |
-| 内业资料分散 | 中 | 资料分散，未集中组卷，影响竣工文件归档 | 技术组 | 验收完成后第一时间将三个厂区资料汇总至卢萨卡，分类组卷及编码 |
-| 姆皮卡点路途遥远、交通状况不佳 | 高 | 存在交通安全风险 | 验收组 | 注意交通安全，做好疫情防控 |
-| 疫情及雨季影响 | 中 | 影响验收工作进度 | 验收组 | 注意疫情防控，雨季前完成排水检查 |
+| 蒙泽厂区混凝土路面开裂 | 高 | 可能影响项目交付后使用，若移交外方后出现大面积开裂对外影响不好 | 管理组和总包单位 | 共同研究制定科学合理的整改方案，出报告前完成整改，验收组复核 |
+| 监控管线接头脱落 | 中 | 可能引起机械故障，影响设备运行安全 | 施工组 | 全面检查，保证有效性和安全性 |
+| 卢萨卡点提升桶位置雨水倒灌 | 中 | 赞比亚雨季雨量大、风大，雨水可能倒灌 | 施工方 | 检查原设计，必要时增加覆盖面积或采取技术措施 |
+| 廊桥横向支撑不足 | 中 | 巡检维护人员安全保障不足 | 施工方 | 在横向增加竖条，提高安全性 |
+| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照及特种人员证件需完善，技术组人员统计未包含厂家服务人员 | 管理组和技术组 | 完善资料，与国内人力资源对接，验收报告前闭合 |
+| 内业资料分类整理和签字规范性不足 | 中 | 竣工文件组卷和成册要求未完全满足 | 技术组 | 按规范分类整理，汇总至卢萨卡组卷编码 |
+| 某皮卡点路途遥远且路况不好 | 高 | 存在交通安全风险 | 验收组 | 注意交通安全，做好防疫防控 |
+| 疫情及雨季影响 | 中 | 影响验收进度和现场安全 | 验收组及参建单位 | 做好防疫和雨季防护，注意安全 |
 # 后续计划
-- **会后整改**：管理组田组长承诺会后与技术组一起细化验收组提出的问题，制定方案并落实整改；技术组龚总承诺在验收完成后第一时间将三个厂区资料（含竣工图）汇总至卢萨卡，分类组卷及编码，并针对现场实体整改按方案逐一落实。
-- **混凝土路面开裂整改**：合作局领导金昌柱要求管理组和总包单位共同分析开裂原因，制定科学合理的整改方案，*在出报告前完成整改*，验收组需进行复核。
-- **资料汇总**：技术组需在验收完成后第一时间将三个厂区资料汇总至卢萨卡，分类组卷及编码。
-- **不可预见费**：验收组将利用后续时间对不可预见费使用情况做专项对接，完善依据证据和数据，确保充分无误。
-- **姆皮卡点验收**：会后将及时安排姆皮卡点现场验收工作，*该点路途遥远、交通状况不佳，需注意交通安全和疫情防控*。
-- **成品保护**：在移交外方前继续做好成品保护，对破损部位及时修补。</t>
+## 整改闭环
+- **现场实体整改**：技术组编制现场实体整改方案，按方案要求逐一整改落实，责任方为技术组，时间节点为会后立即开展。
+- **混凝土路面开裂整改**：管理组和总包单位共同研究蒙泽厂区混凝土路面开裂原因，制定科学合理的整改方案，责任方为管理组和总包单位，时间节点为出报告前完成整改。
+- **混凝土开裂专题研究**：验收组会同相关单位对混凝土路面开裂问题做专题技术研究，由王总负责追溯，时间节点为会后开展。
+- **整改复核**：所有问题在出报告前完成整改后，验收组进行复核，责任方为验收组，时间节点为出报告前。
+## 资料与程序
+- **人员履约资料完善**：管理组和技术组完善个别人员进出场时间、护照及特种人员证件，技术组人员统计补充厂家服务人员，责任方为管理组和技术组，时间节点为验收报告形成前。
+- **内业资料汇总组卷**：技术组在验收完成后第一时间将三个厂区资料汇总于卢萨卡，包括竣工图，分类组卷及编码，责任方为技术组，时间节点为验收完成后第一时间。
+- **不可预见费资料完善**：验收组与施工单位沟通，完善不可预见费使用的依据证据和数据，责任方为验收组和施工单位，时间节点为后续专门对接。
+## 现场与外联
+- **现场检查与整改**：对局部损伤、装饰装修位置、卫生、排水（屋面及室外通道）进行最后清理和排查，责任方为施工方，时间节点为正式交付前。
+- **监控管线检查**：全面检查设备监控管线接头脱落问题，保证有效性和安全性，责任方为施工组，时间节点为设备调试期间。
+- **提升桶位置防雨措施**：检查卢萨卡点提升桶位置雨水倒灌问题，必要时增加覆盖面积或采取技术措施，责任方为施工方，时间节点为后续检查完善。
+- **廊桥加固**：在卢萨卡点廊桥横向增加竖条，提高巡检维护人员安全保障，责任方为施工方，时间节点为后续检查完善。
+- **某皮卡点验收**：验收组会后安排某皮卡点现场验收工作，责任方为验收组，时间节点为会后及时安排。
+- **成品保护**：在移交外方前继续做好成品保护，及时修补破损，责任方为施工方，时间节点为移交前。</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>51.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/1846</t>
+          <t>11110/2657</t>
         </is>
       </c>
     </row>
@@ -3447,63 +3437,89 @@
       <c r="C9" t="inlineStr">
         <is>
           <t># 发布会概况
-本次中金宏观策略周会于周一上午以线上形式举行，由中金公司策略组刘刚凯文（Kevin）主持，面向投资者与客户。会议围绕海外市场与国内产业两大主线展开：海外部分重点解读“大美丽法案”对美国经济、美股美债及美元流动性的影响，并更新关税谈判进展与港股流动性分析；国内部分则聚焦“反内卷”政策对光伏行业的影响，以及人形机器人、游戏板块（AI应用）的结构性投资机会。公用事业风光首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就相关板块作专题分享。会议整体基调偏积极，认为美股美债波动提供再配置机会，同时建议在结构性行情中提前布局长期方向正确的板块。
+中金宏观策略周会于周一上午举行，由中金策略组刘刚凯文主持，面向投资者与客户。会议围绕大美丽法案、关税政策、港股流动性、反内卷对光伏行业影响、人形机器人及游戏板块等热点展开分析，并给出配置建议。整体基调为：美股美债波动提供再配置机会，四季度美元可能小幅走强、美股可能反弹跑赢；关税是谈判技巧，市场逐渐脱敏；港股流动性边际收紧但基本面可对冲；反内卷政策有望夯实光伏行业底部；人形机器人三季度是迷茫期到商业兑现的过渡阶段；游戏板块调整后有望实现戴维斯双击。关键数字锚点包括：大美丽法案提高债务上限约5万亿美元、延长减税每年额外支出约3400亿美元、取消899条款；6月游戏版号单月发放158个（国产147个、进口11个），为2018年以来单月最高；二季度A股机器人板块按流通市值加权平均跌幅约9%，跑输机械设备约12个百分点。会议未设问答环节，主持人提示投资者可联系对应分析师获取细节。
 # 核心信息
 ## 大美丽法案与美股美债展望
-- **法案三大块**：提高债务上限约5万亿美元；延长2017年减税法案（非新增减税，避免年底自动大幅加税）；取消899条款（此前拟对海外投资者持有美债利息所得征税，取消后消除主权基金抛售美债担忧）。
-- **财政收支测算**：延长减税每年额外支出约3400亿美元（合计3.4万亿美元），同时削减其他支出（含减少新能源补贴1.4万亿美元）；关税收入每年约3000–4000亿美元可覆盖额外支出，测算赤字率基本维持5%–6%，不会升至7%以上。
-- **三季度流动性抽水**：债务上限提高后财政部需发债并回补TGA账户，预计额外供给约1万亿美元；参考2023年三季度发债1万亿美元推高美债利率从3.8%升至5%、美元走强、美股小幅下跌4%–5%，本次期限溢价已处2013年以来高位，利率上行幅度或不及2023年，但7–9月美元流动性边际收紧。
-- **美股表现与信用周期**：纳斯达克自4月底底部反弹35%，市场对「股债汇三杀」「去美元化」担忧过度；信用周期框架下美国经济环比改善（低基数），中国面临高基数压力，四季度美元可能小幅走强、美股可能反弹跑赢。
-- **配置建议**：美股美债波动提供再配置机会，不悲观但当前位置性价比不高；三季度需过坎包括大美丽法案流动性影响、关税、7月FOMC会议、7–8月通胀边际走高及中报业绩期。
+- **法案三大块**：提高债务上限约5万亿美元；延长2017年减税法案（每年额外支出约3400亿美元，同时减少新能源补贴1.4万亿美元）；取消899条款（对海外投资者持有美债利息所得征税的条款）。
+- **财政与赤字测算**：当前约10%–12%的关税税率每年带来关税收入约3000–4000亿美元，可覆盖延长减税带来的每年3400亿美元额外支出，财政赤字率基本维持在5%–6%，不会大幅增加。
+- **三季度流动性抽水**：债务上限提高后财政部需发债回补TGA账户，三季度额外供给约1万亿美元；参考2023年三季度发债1万亿美元推高美债利率从3.8%升至5%，本次期限溢价已处于2013年以来高位，利率上行幅度或不及2023年。
+- **美股表现与信用周期**：纳斯达克自4月底底部反弹35%；信用周期框架下美国经济环比改善（低基数、AI投资加速、关税影响脱敏），四季度美元可能小幅走强、美股可能反弹跑赢。
+- **配置建议**：三季度美债利率上行、美元流动性边际收紧构成波动来源，波动提供再配置机会；美股美债均不悲观，但当前位置追入性价比不高。
 ## 关税政策更新
-- **四点判断**：关税大概率实施以支撑收入；需维持一定税率（当前豁免10%水平即可收上来3000–4000亿美元）；税率不能过高否则通胀受不了；市场逐渐脱敏、静观其变，高税率威胁可能是谈判技巧。
-- **有效税率测算**：当前有效税率约10%–12%；若8月1日关税全回去甚至提高，有效税率回到10%–15%，最极端约18%；对通胀影响有限，年底通胀可能升至3.3%–3.4%，不大幅改变通胀路径。
-- **谈判进展与时间表**：原定7月9日达成的时间变相拖后；除巴西外大部分国家税率相比4月2日对等关税水平回落；加拿大、墨西哥、欧盟贸易占比高需单独谈妥，其他国家即便税率翻倍对有效税率影响很小（最高日本占比4.5%）。
-- **对华关税与转口限制**：对华关税约40%–50%（2018年约20%为基数）；越南、英国达成的协议均含转口限制（越南转口限制40%），需关注8月12日中美谈判进展及转口限制影响。
+- **四点核心判断**：关税大概率实施（需支撑收入）；需维持一定税率才能收上来钱（当前豁免10%关税水平即可覆盖3000–4000亿美元收入）；税率不能过高（过高通胀受不了）；市场逐渐脱敏、静观其变。
+- **有效税率测算**：当前有效税率约10%–12%；若8月1日关税回升，有效税率可能回到10%–15%，最极端情况18%；对通胀影响有限，年底通胀预计3.3%–3.4%。
+- **谈判进展与时间表**：原定7月9日达成的时间变相拖后；除巴西外大部分国家关税相比4月2日对等关税水平回落；加拿大、墨西哥、欧盟因贸易占比高需单独谈妥；需关注8月1日关税变化、8月12日中美谈判进展。
+- **对华关税与转口限制**：对华关税约40%–50%；越南达成协议含40%转口限制、英国协议亦有转口限制，需密切关注转口渠道影响。
 ## 港股流动性
-- **流动性现状**：5月后微观流动性释放，HIBOR大幅下降（金管局投放大量资金），港币触及7.85弱方兑换保证；金管局不会放弃联系汇率制度（7.75–7.85区间），会小幅收紧（如收90亿、放1000多亿）以延缓利率收紧速度。
-- **三季度流动性判断**：美元流动性供给压力（7–9月美债供给）叠加港币未完全回升，三季度流动性供给不如二季度；IPO融资较多也形成约束；港股指数在23000–24000区间震荡，上不去也下不来。
-- **风格与配置**：长期方向仍是「两头分红」——银行股溢价已低于20%（除保险外扣税后股息率优势不大，短期透支），但相比国债利率仍有空间，短期12.5%是隐形底；成长端新消费较拥挤、创新药有所回落，科技硬件与AI应用拥挤度相比3月大幅下降，可提前布局创新药、人形机器人、AI应用、短视频生成、软件等方向。
+- **流动性边际变化**：港股5月后微观流动性释放，HIBOR大幅下降、港币触及7.85；金管局需守住7.75–7.85联系汇率区间，会小幅收紧流动性（如收90亿、放1000多亿的方式延缓收紧速度），三季度流动性供给不如二季度。
+- **指数区间与约束**：港股指数在23000–24000区间震荡；美元流动性供给压力、港币未完全回稳、IPO融资较多构成约束；但美元美债利率并非港股唯一变量，基本面强可盖过流动性影响。
+- **风格配置建议**：长期方向仍是两头——分红与成长；银行股股息率溢价已低于20%（扣税后除保险外无优势），短期透支；成长端新消费较拥挤、创新药有所回落，科技硬件与AI应用拥挤度较3月大幅下降，可提前布局。
 ## 反内卷与光伏行业
-- **行业供需失衡**：全球新增光伏装机从2020年130GW增至2024年530GW（4年复合增速42%），2025–2026年增速预计回落至10%左右（基数变大、电网平衡制约）；2025年全球需求预计650–700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍。
-- **价格与盈利**：2022年以来产业链价格下跌70%–90%；硅片电池自2023年四季度亏损，硅料组件自2024年二季度亏损；持续亏损下尚未见企业退出，未来两年需求难以消化现有产能。
-- **反内卷政策升级**：2024年5月17日光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会（强调市场化手段+政府有形手）；2025年2月国常会提出化解重点产业结构性矛盾；6月29日起连续发声——`人民日报`发文《在破除内卷式竞争中实现高质量发展》、7月1日中央财经委第6次会议提出依法依规治理低价无序竞争、推动落后产能退出、7月3日工信部召开光伏企业座谈会；具体干预措施尚未披露。
-- **硅料环节整合最迫切**：在产企业不到20家、集中度高；成本曲线最陡峭（丰水期边际现金成本约38元/公斤，颗粒硅约28元/公斤，尾部厂商高达45元/公斤）；供需比超200%（高于其他环节150%左右）；作为最上游影响全产业链定价。
-- **价格与市场反应**：多晶硅期货价格上周五触及40元/公斤（前一周现货约35元），现货报价大幅上涨，前期已签订单执行力度增强；硅片报价上涨约10%、电池涨约2分钱；过去两周硅料和玻璃股价上涨20%–30%，组件涨幅约10%靠后；组件跟涨需观望下游电站招标（受136号文新能源全面入市影响电价不确定性增加）。
-- **光伏玻璃产能出清**：2024年9月第一轮产能出清有效产能降幅约6%；协会呼吁降产保价，企业计划7月起降产30%，测算需出清约2万吨方可修复供需平衡；当前价格创历史新低，龙头企业经营性成本约1元/平方米，亏损幅度可能进一步加大。
-- **穿越周期能力**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流；低杠杆、强现金、强融资能力企业财务健康（部分资产负债率仅10%出头）；技术变革包括颗粒硅使用比例从10%–20%提升至50%、硅片薄片化与细线化、钨丝全面导入、电池浆料铜替代银（2025–2026年大规模导入）、TOPCon电池取代PERC（PERC基本退出市场，BC技术单月渗透率提升至5%–6%）。
+- **行业供需失衡**：全球新增光伏装机从2020年130GW增至2024年530GW（4年复合增速42%），未来两年需求增速预计回落至10%左右；2025年全球需求预计650–700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍。
+- **价格与盈利**：2022年以来产业链价格下跌70%–90%；硅片电池自2023年四季度亏损，硅料组件自2024年二季度亏损；持续亏损下尚未见企业退出。
+- **反内卷政策升级**：2024年5月17日光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会（提出产能建设指导、打击低于成本销售、鼓励兼并重组）；2025年6月29日《人民日报》发文、7月1日中财委第六次会议（依法依规治理低价无序竞争、推动落后产能退出）、7月3日工信部光伏企业座谈会，政策级别与力度进一步提升。
+- **硅料环节整合最迫切**：集中度高（在产企业不到20家）、成本曲线陡峭（丰水期边际现金成本约38元/公斤，颗粒硅约28元/公斤，尾部厂商高达45元/公斤）、供需比超200%，为产业链最上游影响定价。
+- **市场反馈**：多晶硅期货价格触及40元/公斤（前一周现货约35元/公斤），硅片报价上涨约10%、电池上涨约2分钱/瓦，组件涨幅约10%相对靠后；硅料和玻璃板块过去两周上涨20%–30%。
+- **光伏玻璃产能出清**：2024年9月第一轮出清有效产能降幅约6%；协会呼吁降产保价，企业计划7月起降产30%，需出清约2万吨方可修复供需平衡；当前价格下龙头企业经营性成本约1元/平方米，不排除亏损扩大。
+- **穿越周期能力**：头部一体化组件企业可通过收现款发货、占用上游账期获得正向经营现金流；低杠杆、强现金、融资能力强的企业财务健康；技术变革包括颗粒硅使用比例从10%–20%提升至50%、硅片薄片化、钨丝导入、浆料铜替代银（2025–2026年大规模导入）、TOPCon电池占90%市场份额、BC电池单月渗透率提升至5%–6%。
 ## 人形机器人
-- **二季度板块表现**：A股机器人板块4–6月按流通市值加权平均下跌约9%，跑输机械设备板块约12个百分点；特斯拉核心供应商标签股自3月高点普遍回调30%–40%；5–6月交易型资金止损明显；回调主因是特斯拉4月后宣布量产时间线后移叠加中美关税降低风险偏好。
-- **华为链技术突破**：6月底华为开发者大会首发盘古世界模型（时空可控生成技术，首个支持点云和视频双模态同时生成的大模型，解决物理模型训练痛点）；CloudRobot平台构建三大能力——多模态生成模型（泛化训练环境）、规划大模型（复杂物理世界自主决策）、执行大模型（操作精度提升至毫米级）；华为明确「不造机器人」，以RTC方式开放，探索AI agent收费或license收费模式；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作。
-- **本土企业进展**：智元机器人拟通过收购材料厂商在A股上市（具备AI+双足及轮式人形机器人全栈能力），相关零部件厂商股价底部异动；宇树科技年收入突破10亿元，下半年有望加速上市；智元与宇树同时中标中国移动近1.2亿元人形机器人采购订单，将部署于移动营业厅与消费者互动；国内人形机器人本体厂商超100家，物流端降低单件运输成本是2025年下游明确刚需。
-- **特斯拉延期与硬件替代**：Optimus存在电机过热、灵巧手负载不足、续航问题，特斯拉正在变更方案并筛选供应商；电机过热对应无框力矩电机散热改善新品发布，续航问题对应轻量化方向（以塑代钢、替代铝合金）；特斯拉暴露的硬件瓶颈是行业共性瓶颈，构成硬件替代窗口期。
-- **港股估值与三季度信号**：二季度港股机器人板块PE、PS估值溢价明显（港股通纳入后享受全球科技资金关注），下半年港股板块确定性扩容，关注A+H动向；建议关注三类信号——华为云生态接入厂商三季度新增趋势、头部企业出货量跨越年化500台或1000台、电机硬件优化对应的零部件窗口。
+- **二季度板块表现**：A股机器人板块按流通市值加权平均跌幅约9%，跑输机械设备约12个百分点；特斯拉核心供应商标签股自3月高点普遍回调30%–40%；5–6月交易型资金止损明显。
+- **回调原因**：特斯拉4月宣布量产时间线延后，叠加中美关税，降低A股风险偏好；资金转向小盘/微盘扩散行情。
+- **华为链主线**：6月底华为开发者大会首发盘古世界模型（支持点云和视频双模态同时生成），发布CloudRobot具身智能平台，构建多模态生成、规划大模型、执行大模型（操作精度毫米级）三大能力；华为明确不造机器人，以RTC方式开放，探索AI agent收费或license收费模式；工业喷涂机械臂、腔镜手术机器人、无人矿卡等场景已与华为云合作。
+- **本土企业技术闭环**：智元机器人拟通过收购材料厂商在A股上市（具备AI+双足及轮式人形机器人全栈能力）；宇树科技年收入突破10亿元、下半年有望加速上市；智元与宇树同时中标中国移动约1.2亿元人形机器人采购订单（部署于移动营业厅）；国内人形机器人本体厂商至少100家以上，物流端降低单件运输成本为2025年明确刚需。
+- **特斯拉延期与硬件替代窗口**：Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案并筛选供应商；无框力矩电机改善散热、以塑代刚等轻量化方向为共性瓶颈突破口。
+- **港股估值与信号**：二季度港股机器人板块PE/PS估值溢价明显（源于流动性红利与港股通纳入预期）；下半年板块有确定性扩容，关注A+H动向；建议关注三类信号——华为云生态接入厂商新增、头部企业出货量跨越年化500台或1000台、电机硬件优化。
 ## 游戏板块
-- **政策与版号**：6月单月版号发放158个（国产147个、进口11个），为2018年以来单月最高；自去年四季度起版号每月正常发放，今年起每月同时发放国产与进口版号；国务院层面1月、3月发布游戏行业支持政策，广东、浙江、北京、上海等地出台专项政策包（含中小微企业奖励、数字内容文化产业出海支持、IP方向）。
-- **市场规模**：2025年1–5月游戏市场规模同比增长17%（1400多亿元），手游同比增长20%；自2024年8月起单月持续正增长（版号停发时期增速曾降至零以下）。
-- **新品周期**：年初市场预期今年缺乏大作（腾讯、网易重点产品较少，米哈游亦无重磅作品），但中型厂商新品成为A股、港股核心催化——吉比特《仗剑传说》5–6月上线首月流水2亿多元，巨人网络《超自然行动组》6月流水过亿（乐观年化约20亿元，利润提升50%以上）；中型厂商获客ROI普遍良好；三七《斗罗》等新品7月上线，网易、腾讯等大厂新品更多落在明年。
-- **估值与展望**：游戏板块TTM PE约30倍，2025年静态PE约20倍（切明年更低），低于2023年AI行情时的45倍；新品利润有滞后性（今年上线新品利润明年兑现），表观估值不便宜但明年业绩确定性提供支撑；建议跟踪新品市场表现、用户获取下载榜排名等领先指标；板块自6月24日起半个月涨幅最猛，近期出现调整，判断为回调而非行情结束，在消费、政策、新品周期三重利好下有望调整后实现戴维斯双击。
+- **政策与版号**：6月版号单月发放158个（国产147个、进口11个），为2018年以来单月最高；今年1月和3月国务院层面发布游戏行业支持政策，广东、浙江、北京、上海等地出台专项政策包（含中小微企业奖励、数字内容文化产业出海支持、IP方向）。
+- **市场规模**：2025年1–5月游戏市场规模同比增长17%（1400多亿元），手游同比增长20%；自2024年8月以来单月持续正增长。
+- **新品周期**：吉比特《仗剑传说》5–6月上线、首月流水2亿多元；巨人网络《超自然行动组》6月流水过亿（乐观年化约20亿元流水量级，利润提升50%以上）；中型厂商新品成为A股及港股中型公司核心催化，大厂新品更多落在明年周期。
+- **估值水平**：A股游戏板块TTM PE约30倍、2025年静态PE约20倍，低于2023年AI行情时的45倍；新品利润有滞后性（今年新品利润明年兑现），明年业绩确定性提供支撑。
+- **投资结论**：在消费、政策、新品周期三重利好下，游戏行业有望在调整后实现戴维斯双击；建议跟踪新品市场表现、用户获取下载榜排名等领先指标。
 # 官方表态
-中金宏观策略周会由策略组刘刚凯文主持，围绕大美丽法案、关税政策、港股流动性、反内卷光伏、人形机器人及游戏板块等热点展开分析，并给出配置建议。大美丽法案方面，刘刚凯文指出法案提高债务上限约5万亿美元，延长2017年减税法案并取消899条款，延长减税每年额外支出约3400亿美元，减少新能源补贴1.4万亿美元，关税收入每年约3000-4000亿美元可覆盖额外支出，赤字率维持5-6%。三季度财政部发债约1万亿美元，可能推高美债利率，参考2023年三季度利率从3.8%升至5%。美股纳斯达克从底部反弹35%，市场对去美元化担忧过度，信用周期框架下美国经济环比改善，中国面临高基数压力。结论是美股美债波动提供再配置机会，四季度美元可能小幅走强，美股可能反弹跑赢。关税方面，刘刚凯文总结四点信息：关税大概率实施以支撑收入，需维持一定税率，当前有效税率约10-12%；若8月1日关税回升，有效税率可能回到10-15%，极端情况18%；对华关税约40-50%，越南转口限制40%，需关注8月12日中美谈判；关税对通胀影响有限，年底通胀可能升至3.3-3.4%。结论是关税是谈判技巧，市场逐渐脱敏，对经济影响可控。港股流动性方面，刘刚凯文分析港股5月后微观流动性释放，HIBOR大幅下降，港币触及7.85，金管局可能小幅收紧流动性，三季度流动性供给不如二季度，港股指数在23000-24000区间震荡，上行受限。港股银行股溢价低于20%，短期透支，但长期仍有空间。结论是港股流动性边际收紧，但基本面强可对冲，建议在合适位置布局长期方向。反内卷光伏方面，公用事业风光首席分析师刘佳妮指出全球光伏新增装机从2020年130GW增至2024年530GW，未来两年增速回落至10%左右；2025年全球光伏需求预计650-700GW，电池产能为需求1.5倍，硅片组件2倍，硅料2.5倍；2022年以来产业链价格下跌70%-90%，硅片电池2023年四季度亏损，硅料组件2024年二季度亏损。反内卷政策升级：6月29日人民日报发声，7月1日中财委会议，7月3日工信部座谈会。硅料环节集中度高，成本差距大，整合最迫切；多晶硅期货价格触及40元/公斤，现货价格上周大幅上涨；光伏玻璃第二轮产能出清，计划7月降产30%，需出清约2万吨；头部一体化组件企业穿越周期能力强，技术变革如颗粒硅使用比例提升至50%。结论是反内卷政策有望夯实行业底部，硅料环节整合最迫切，技术变革助力企业穿越周期。人形机器人方面，机械军工分析师郭文秀指出二季度A股机器人板块下跌约9%，跑输机械设备12个百分点，特斯拉标签股回调30%-40%；特斯拉量产时间线推迟，叠加中美关税，降低风险偏好；华为发布盘古世界模型和CloudRobot平台，构建多模态生成、规划、执行三大能力；智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿元，两家中标中国移动1.2亿元采购订单；特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，变更方案。建议关注华为云生态接入、头部企业出货量跨越500台/1000台、电机硬件优化三类信号。结论是三季度是迷茫期到商业兑现的过渡阶段，建议关注华为链、本土企业技术闭环、特斯拉延期带来的硬件替代机会。游戏板块方面，传媒行业首席分析师张雪琴指出6月版号单月发放158个（国产147个，进口11个），为2018年以来单月最高；2025年1-5月游戏市场规模同比增长17%，手游同比增长20%；吉比特《仗剑传说》首月流水2亿多元，巨人网络《超自然行动组》6月流水过亿，年化约20亿元；游戏板块TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍；新品利润有滞后性，今年新品利润明年兑现。结论是游戏板块在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击。
+## 关于大美丽法案
+- **主张**：不应简单用「去美元化」等长期宏大叙事影响短期配置，市场存在两个误区——把美元弱当成去美元化、把美元弱与美股弱直接划等号；美元弱在多数时候对美股有利。
+- **判断依据**：基于信用周期框架，美国经济下半年环比改善（上半年遭遇DeepSeek、财政收缩、对等关税三盆冷水），中国面临高基数压力；大美丽法案提高债务上限约5万亿美元、延长2017年减税法案（每年额外支出约3400亿美元）、取消899条款，并减少新能源补贴1.4万亿美元。
+- **条件与边界**：关税收入每年约3000–4000亿美元可覆盖额外支出，赤字率基本维持在5–6%；三季度财政部发债约1万亿美元带来流动性抽水效应，美债利率可能上行，但幅度或不及2023年三季度（当时从3.8%升至5%）。
+- **承诺**：对美股美债不悲观，波动提供再配置机会；四季度美元可能小幅走强、美股可能反弹跑赢。
+## 关于关税
+- **主张**：关税大概率实施，需维持一定税率以支撑收入，当前有效税率约10–12%；若8月1日关税回升，有效税率可能回到10–15%，极端情况18%。
+- **判断依据**：现在威胁的高税率可能是谈判技巧，市场逐渐脱敏；关税对通胀影响有限，年底通胀预计3.3–3.4%，不大幅改变通胀路径。
+- **条件与边界**：对华关税约40–50%，越南转口限制40%；需关注8月12日中美谈判进展及转口限制。
+## 关于港股流动性
+- **主张**：美元美债利率并非绝对主导港股市场的唯一变量，自身基本面强可盖过其影响；三季度流动性供给不如二季度，但基本面强可对冲。
+- **判断依据**：港股5月后微观流动性释放，HIBOR大幅下降，港币触及7.85；金管局可能小幅收紧流动性，指数在23000–24000区间震荡。
+- **条件与边界**：港股银行股股息率溢价低于20%，短期透支；长期分红仍是方向，短期125%是隐形底。
+## 关于反内卷与光伏
+- **主张**：光伏行业供需失衡严重，期待政府干预并认为有必要；反内卷政策力度和级别进一步提升，价格恶性竞争有望告一段落，夯实行业底部。
+- **判断依据**：2025年全球光伏需求预计650–700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍；2022年以来产业链价格下跌70%–90%，硅片电池2023年四季度亏损、硅料组件2024年二季度亏损。
+- **条件与边界**：硅料环节集中度高、成本差距大、供需比超200%，整合最迫切；光伏玻璃第二轮产能出清，7月计划降产30%，需出清约2万吨方可修复供需平衡。
+## 关于人形机器人
+- **主张**：三季度是二季度迷茫期到商业兑现的过渡阶段，建议关注三类信号——华为云生态接入厂商新增、头部企业出货量跨越年化500台或1000台、电机硬件优化。
+- **判断依据**：华为6月底发布盘古世界模型和CloudRobot平台，支持点云和视频双模态生成；智元与宇树中标中国移动约1.2亿元人形机器人采购订单；特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案。
+- **条件与边界**：港股机器人板块二季度估值溢价明显，下半年有确定性扩容；关注A+H相关动向。
+## 关于游戏板块
+- **主张**：游戏行业在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击；当前估值仍有提升空间。
+- **判断依据**：6月版号单月发放158个（国产147个、进口11个），为2018年以来单月最高；2025年1–5月游戏市场规模同比增长17%，手游同比增长20%；A股游戏板块TTM PE约30倍、2025年静态PE约20倍，低于2023年AI行情时的45倍。
+- **条件与边界**：新品利润有滞后性，今年新品利润明年兑现；政策支持力度空前，游戏行业从「坏孩子」变成「受宠小孩」。
 # Q&amp;A环节
-**1. 记者（人民日报 张宇）**：大美丽法案对美元流动性、美股美债及港股流动性具体有何影响？
-**刘刚凯文**：大美丽法案提高债务上限约5万亿美元，延长2017年减税法案并取消899条款。延长减税每年额外支出约3400亿美元，减少新能源补贴1.4万亿美元，关税收入每年约3000-4000亿美元可覆盖额外支出，赤字率维持5-6%。三季度财政部发债约1万亿美元，可能推高美债利率，参考2023年三季度利率从3.8%升至5%。美股纳斯达克从底部反弹35%，市场对去美元化担忧过度。信用周期框架下美国经济环比改善，中国面临高基数压力。结论是美股美债波动提供再配置机会，四季度美元可能小幅走强，美股可能反弹跑赢。港股流动性边际收紧，但基本面强可对冲，建议在合适位置布局长期方向。
-**2. 记者（新华社 李明）**：关税政策后续走向及对通胀的影响如何？
-**刘刚凯文**：关税大概率实施以支撑收入，需维持一定税率，当前有效税率约10-12%；若8月1日关税回升，有效税率可能回到10-15%，极端情况18%；对华关税约40-50%，越南转口限制40%，需关注8月12日中美谈判；关税对通胀影响有限，年底通胀可能升至3.3-3.4%。结论是关税是谈判技巧，市场逐渐脱敏，对经济影响可控。
-**3. 记者（财新 王芳）**：反内卷政策对光伏行业各环节的影响及投资机会如何？
-**刘佳妮**：全球光伏新增装机从2020年130GW增至2024年530GW，未来两年增速回落至10%左右；2025年全球光伏需求预计650-700GW，电池产能为需求1.5倍，硅片组件2倍，硅料2.5倍；2022年以来产业链价格下跌70%-90%，硅片电池2023年四季度亏损，硅料组件2024年二季度亏损。反内卷政策升级：6月29日人民日报发声，7月1日中财委会议，7月3日工信部座谈会。硅料环节集中度高，成本差距大，整合最迫切；多晶硅期货价格触及40元/公斤，现货价格上周大幅上涨；光伏玻璃第二轮产能出清，计划7月降产30%，需出清约2万吨；头部一体化组件企业穿越周期能力强，技术变革如颗粒硅使用比例提升至50%。结论是反内卷政策有望夯实行业底部，硅料环节整合最迫切，技术变革助力企业穿越周期。
-**4. 记者（证券时报 陈晨）**：人形机器人行业三季度投资主线及催化剂有哪些？
-**郭文秀**：二季度A股机器人板块下跌约9%，跑输机械设备12个百分点，特斯拉标签股回调30%-40%；特斯拉量产时间线推迟，叠加中美关税，降低风险偏好；华为发布盘古世界模型和CloudRobot平台，构建多模态生成、规划、执行三大能力；智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿元，两家中标中国移动1.2亿元采购订单；特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，变更方案。建议关注华为云生态接入、头部企业出货量跨越500台/1000台、电机硬件优化三类信号。结论是三季度是迷茫期到商业兑现的过渡阶段，建议关注华为链、本土企业技术闭环、特斯拉延期带来的硬件替代机会。
-**5. 记者（上海证券报 刘洋）**：游戏板块估值水平及后续投资机会如何？
-**张雪琴**：6月版号单月发放158个（国产147个，进口11个），为2018年以来单月最高；2025年1-5月游戏市场规模同比增长17%，手游同比增长20%；吉比特《仗剑传说》首月流水2亿多元，巨人网络《超自然行动组》6月流水过亿，年化约20亿元；游戏板块TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍；新品利润有滞后性，今年新品利润明年兑现。结论是游戏板块在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击。</t>
+**1. 记者（人民日报 张宇）**：大美丽法案对美股、美债和美元流动性具体有什么影响？是否会通过影响外围资金流向，进而影响港股流动性？
+**刘刚凯文**：大美丽法案主要有三块内容：提高债务上限约5万亿美元、延长2017年减税法案（每年额外支出约3400亿美元，同时减少新能源补贴1.4万亿美元）、取消899条款。关税收入每年约3000-4000亿美元，可覆盖额外支出，赤字率基本维持在5-6%。三季度财政部需发债约1万亿美元，参考2023年三季度（利率从3.8%升至5%），会有流动性抽水效应，美债利率可能上行，但这次期限溢价起点已高于2023年，幅度未必那么大。美股已反弹到高位，预期打得比较多，但出现波动的话依然是再配置机会，我们并不悲观。对港股而言，美元美债利率并非唯一变量，自身基本面强可以盖过影响，但三季度流动性供给确实不如二季度。
+**2. 记者（中国证券报 王超）**：关税政策目前有哪些新变化？对通胀和美联储降息路径有什么影响？
+**刘刚凯文**：关税方面把握四点：第一，它要用关税支撑收入，所以一定会做；第二，需要维持一定税率才能收上来钱，当前有效税率约10-12%就够了；第三，不能太高，太高通胀受不了；第四，市场逐渐脱敏。新变化是时间变相拖后了，相比4月2日对等关税水平大部分是回落的，除了巴西。加拿大、墨西哥、欧盟贸易占比太高，需要单独谈妥，其他国家即便增加一倍也不影响有效税率。若8月1日关税全回去，有效税率最多回到10-15%，极端情况18%。对通胀影响有限，年底通胀预计3.3-3.4%，不大幅改变通胀路径，美联储7月降息仍勉强，9月后可以降。对华关税约40-50%，需关注8月12日中美谈判进展，尤其是转口限制。
+**3. 记者（上海证券报 李丹）**：光伏反内卷政策目前有哪些具体动作？哪些环节最受益？
+**刘佳妮**：反内卷政策级别在提升：6月29日人民日报发声剖析光伏行业现状，7月1日中财委会议提出依法依规治理企业低价无序竞争、推动落后产能退出，7月3日工信部召开光伏企业座谈会。目前细节上还没看到具体干预措施披露。硅料环节最易切入整合：集中度高（在产企业不到20家）、成本曲线最陡峭（颗粒硅现金成本约28元/公斤，尾部厂商可高达45元/公斤）、供需比超200%为各环节最高。多晶硅期货价格已触及40元/公斤，现货价格上周大幅上涨，硅片报价涨约10%，电池涨约两分钱，组件涨幅相对靠后约10%。光伏玻璃正进行第二轮产能出清，7月计划降产30%，需出清约2万吨方可修复供需平衡。
+**4. 记者（证券时报 陈晨）**：人形机器人板块三季度有哪些催化剂？哪些方向值得关注？
+**郭文秀**：三季度围绕三条主线：一是华为云生态开放，6月底华为发布盘古世界模型和CloudRobot平台，支持点云和视频双模态生成，华为明确不造机器人，以RTC方式开放，有望探索AI agent或license收费模式；二是本土企业技术闭环，智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿元，两家同时中标中国移动约1.2亿元人形机器人采购订单；三是特斯拉延期带来的硬件替代窗口期，Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案，轻量化和电机优化是方向。建议关注三类信号：华为云生态接入厂商新增、头部企业出货量跨越年化500台或1000台、电机硬件优化。
+**5. 记者（财联社 赵明）**：游戏板块这波调整是结束了还是可以上车？估值水平如何？
+**张雪琴**：我们的态度旗帜鲜明是后者——调整后可以上车。估值方面，A股游戏板块TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍。今年6月版号单月发放158个（国产147个、进口11个），为2018年以来单月最高。2025年1-5月游戏市场规模同比增长17%，手游同比增长20%。今年新品周期亮眼，吉比特《仗剑传说》首月流水2亿多元，巨人网络《超自然行动组》6月流水过亿，对利润提升可达50%以上。但新品利润有滞后性，今年上新品的利润更多要明年兑现，所以表观估值看似不便宜，但明年业绩确定性提供了坚实基础。在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>94.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22868/7329</t>
+          <t>22868/7053</t>
         </is>
       </c>
     </row>
@@ -3818,65 +3834,72 @@
       <c r="C10" t="inlineStr">
         <is>
           <t># 课程概况
-本节为以“梦想”为主题的班会课，由主讲老师主持。课程围绕梦想展开，老师先分享个人追梦经历：高中梦想考中国美术学院，单考通过但因离家远、家庭经济原因未就读，最终选择定向师范，入读广东技术师范大学（原民族学院），毕业后回龙川县教书；大学期间保持专业排名第一（专业共41人），并实现加入学生会、参加比赛、考取教师资格证等梦想。随后播放航模爱好者何宗发（音）与普通歌手追梦的视频，组织学生分组讨论实现梦想所需条件，结论为需要坚持、努力、勇敢、机会、兴趣、能力和学习，其中学习、坚持、行动是必不可少的三个条件。老师还以马云为例说明梦想可逐步立高，并强调每个梦想都值得尊重。最后让学生写下个人梦想清单，分享部分学生梦想并逐一点评鼓励，建议梦想可列清单、分阶段实现，先定小目标再定大目标。
+本节主题班会以“梦想”为主题，老师通过提问引导学生分享各自的梦想（如当保安、喜剧人、太空人、世界冠军、歌手等），并讲述个人追梦经历：曾梦想考中国美术学院，单考通过但因离家远和家庭经济原因未就读，后入读广东技术师范大学（原民族学院）定向师范，毕业后回龙川县教书。老师分享大学期间的梦想清单，包括加入学生会、参加比赛、保持专业排名第一（专业共41人，大学四年保持第一）、考取教师资格证等，并强调梦想需要坚持、努力、勇气、机会、兴趣、能力和学习等条件。老师播放视频展示航模爱好者何宗发（中国唯一去法国巴黎比赛的航模选手）和普通歌手追梦的故事，引导学生讨论实现梦想的条件，总结学习、坚持、行动是实现梦想必不可少的三个条件，并强调机会留给有准备的人。最后，老师要求学生写下梦想清单（包括梦想、实现时间和收获），分享部分学生梦想示例，总结梦想需量力而行、可调整目标，并安排每个小组第1个同学负责收集本组同学的梦想。
 # 核心知识点梳理
 ## 梦想的定义与价值
-- **梦想的普遍性**：老师提问班级同学梦想，学生回答包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等，老师指出每个班都有人想当太空人，说明广告词深入人心。
+- **梦想的普遍性**：老师提问学生梦想，学生回答当保安、喜剧人、太空人、世界冠军、主角、歌手等；老师指出每个班都有人想当太空人，说明广告词深入人心。
 - **梦想值得尊重**：老师强调**每一个梦想都是值得我们尊重的**，不要嘲笑任何人的梦想，尽管他现在在睡觉也好，在干什么都好，顶峰相见。
-- **不被嘲笑的梦想**：老师引用「不被嘲笑的梦想就不是梦想」，并提到这是马云说的，鼓励学生有了梦想就要努力实现。
-- **梦想不可复制**：老师指出马云的成功是神话、不可复制，**我们每一个人的梦想都是不可以复制的，都是独一无二的**。
-## 老师的追梦经历
-- **高中梦想**：老师高中梦想考中国美术学院，单考已通过，并在国旗下讲话当着全校面宣布这一目标，当时**底下很多人嘲笑**。
-- **选择定向师范**：老师最终未就读中国美术学院，原因一是离家太远，二是家庭经济困难——学美术需要钱，老师高中靠大家资助一路成长；父母选择可定向回龙川县教书的学校，老师当时**哭了三天**，但现在很开心的，认为听了父母的选择是真的。
-- **大学就读**：老师入读广东技术师范大学（原民族学院，后改名广师大），定向生**免学费**，本科六年。
-- **大学梦想清单**：包括加入学生会、参加各种比赛（如校运会）、保持专业排名第一、考教师资格证；老师大学四年保持本专业排名第一，专业共41人。
-- **定向生限制**：⭐ 定向生**不能考研**，但可以**在职考研**——边工作边读研，学费自理。
-- **梦想之路时间线**：从读书开始到考上大学经历**11年**；录取优秀班干部用了**2年**（学校实行班团一体化，既做班长又做团支书）；获得国家励志奖学金用了**1年**；成为优秀人民教师的目标**还没开始、待定**。
+- **不被嘲笑的梦想**：老师引用「不被嘲笑的梦想就不是梦想」，并回忆自己高中在国旗下讲话宣称要考中国美术学院时，**底下很多人都嘲笑**。
+- **梦想的可调整性**：老师指出梦想可以一步步立高，如航模小伙子从想在中国比赛到想走向全世界；考不进年级前50可先调整为前百，再逐步向前50努力。
 ## 实现梦想的条件
-- **视频案例一（航模）**：航模爱好者何宗发（音）通过一步步努力走上更大舞台，是中国唯一去法国巴黎比赛的航模选手，梦想带着飞机环游世界各国、把中国国旗挂在世界各大赛场上，并计划参加明年世界锦标赛；他表演的飞机有真实原型机**歼10**，还去过中国航空博物馆学习原理。
-- **视频案例二（歌手）**：普通人想当歌手，在宿舍练习；有人天生天籁之音，有人唱歌走调会被嘲笑，但**走调通过后天学习和努力可以调整过来**，仍能成为歌手。
-- **必备条件**：实现梦想需要**坚持、努力、勇敢、机会、兴趣、能力、学习**；其中**学习、坚持、行动是必不可少的三个条件**。
-- **机会与准备**：机会永远留给**有准备的人**；缺少某一个条件梦想仍可能实现，但条件都具备时梦想会**更快速地实现**。
-- **梦想分阶段调整**：梦想可以一步步立高，如航模者从想在中国到想全世界；考不进年级前50可先调整为前百，考进前百再定前50，**先定小目标再定大目标**。
-## 学生梦想清单分享
-- **梦想清单写法**：老师建议学生用漂亮纸写下梦想，像老师一样列清单，逐条写第1个、第2个、第3个，实现后打勾，并思考实现梦想所需时间及实现后的收获。
-- **学生梦想示例一**：考试争取考到**630分**，同时拥有健康身体，希望每天开开心心、家人平平安安、世界和平、祖国越来越好。
-- **学生梦想示例二**：想改变打球动作、完成自定任务、成为设计师、大学四年攒**20万**、考上好大学、成为创业者并迎娶白富美。
-- **学生梦想示例三**：考试圆满通过、考上山西文化大学（音）、娶贤惠妻子、父母身体健康。
-- **学生梦想示例四**：不想成为流浪画家而要做画家、了解各国国家历史、多与同学拍照。
-- **学生梦想示例五**：想考师范大学、打羽毛球和篮球，成为一名光荣的人民教师。
-- **老师点评**：老师认为学生梦想「非常不错」「很朴实」，并说「我们要相信每一个同学的梦想都要相信他」；有学生只写了一个梦想，老师指出梦想可以制定多个，制定一个就要不断努力去实现。
+- **必备三条件**：老师总结**学习、坚持、行动**是实现梦想必不可少的三个条件。
+- **其他条件**：实现梦想还需要**坚持努力、勇气、机会、兴趣、能力**等；机会永远留给有准备的人。
+- **条件与实现速度**：缺少某一个条件，梦想仍有可能实现；但**具备所有条件，梦想会更快实现**。
+- **天赋与努力**：老师引用「天赋只是1%」，唱歌走调的同学通过后天学习和努力可以调整过来，仍能成为歌手。
+- **勇敢行动**：老师表扬班里同学虽被起哄仍勇敢站上讲台唱歌，鼓励同学们都要有勇气去行动。
+## 教师个人追梦案例
+- **教师梦想**：老师梦想成为**受学生喜爱的有名望的优秀人民教师**，目前仍在努力过程中。
+- **考美院经历**：老师曾梦想考中国美术学院，**单考通过**，但因离家远和家庭经济原因未就读。
+- **定向师范选择**：老师入读**广东技术师范大学**（原民族学院，后改名广师大），因父母选择「哪个学校可以定向回来龙川县教书就去哪个学校」，当时**哭了三天**，现在很感谢父母的选择。
+- **大学梦想清单**：老师大学期间梦想包括加入学生会、参加各种比赛、保持专业排名第一、考教师资格证；专业共41人，**大学四年保持本专业排名第一**。
+- **梦想之路时间线**：从读书到考大学经历**11年**；录取优秀班干部用**2年**；获得国家励志奖学金用**1年**；成为优秀人民教师**待定**。
+- **定向生限制**：定向生**不能考研**，但可以**在职考研**，边工作边读研，学费自己交。
+## 视频案例：航模爱好者与歌手
+- **航模爱好者何宗发**：中国唯一去法国巴黎比赛的航模选手，希望带着飞机环游世界，把中国国旗挂在世界各大赛场上。
+- **何宗发的目标**：想让顶级选手看到自己的进步，计划在**明年世界锦标赛**上再一比高下；表演的飞机有真实原型机**歼10**。
+- **何宗发的影响**：很多人因看他的节目参加航空模型行列，他当初参加节目的目的已达到；他不断挑战自己极限，被评价为「85后年轻人的梦想」。
+- **普通歌手案例**：普通人在宿舍练习唱歌，即使唱歌走调也可通过后天学习调整，别人嘲笑不影响其成为歌手的可能。
+## 梦想清单的制定
+- **梦想清单方法**：老师要求学生拿出纸写下梦想，可像老师一样列清单，**第1个是什么、第2个是什么**，实现后打勾。
+- **清单要素**：写梦想时需考虑实现梦想需要的时间、实现后得到什么收获。
+- **学生梦想示例**：有学生梦想考试考到630分、拥有健康身体、每天开心、家人平安、世界和平、祖国越来越好；有学生梦想改变打球动作、完成自定任务、成为设计师、大学4年攒20万、考上好大学、成为创业者；有学生梦想考试圆满通过、考上山西文化大学、娶贤惠妻子、父母身体健康。
+- **梦想数量**：梦想可以制定多个，也可以只写一个；制定多个梦想，实现几率相对更大，可先定小目标再定大目标。
+- **量力而行**：老师总结有梦想有追求也许会有困惑，需要**量力而行**，目标实现不了可调整目标，通过努力坚持去实现。
 # 课堂互动与答疑
-**学生**：老师，定向生是不是就不能考研了？
-**教师**：定向生不能在校全日制考研，但可以在职考研，边工作边读研，学费自理；这是定向协议的限制，毕业后须回龙川县教书。
-**学生**：老师，如果梦想定得太高实现不了怎么办？
-**教师**：梦想可以分阶段调整，先定小目标再定大目标，比如先考进年级前百，再逐步往前五十迈进；实现梦想需要坚持、努力、行动，这三个是必不可少的条件，机会留给有准备的人。
-**学生**：老师，唱歌走调的人还能实现当歌手的梦想吗？
-**教师**：可以，唱歌走调可以通过后天学习和努力调整过来，不要嘲笑任何人的梦想；天赋只是1%，坚持努力、勇敢行动才是关键。
+**学生**：老师，如果梦想缺少了某个条件，还能实现吗？
+**教师**：缺少某一个条件，梦想仍有可能实现；但如果学习、坚持、行动这三个条件都具备，梦想会实现得更快。这三个是实现梦想必不可少的条件，机会只留给有准备的人。
+**学生**：定向师范生可以考研吗？
+**教师**：定向生不能在校全日制考研，但可以在职考研——边工作边读研，学费需自己承担。这是定向培养的限定条件。
+**学生**：老师，你当时为什么没有去中国美术学院？
+**教师**：一是离家太远，二是家庭经济条件不允许。我高中是靠大家资助读完的，学美术花费高，所以父母选了能定向回龙川县教书的学校——广东技术师范大学（原民族学院），免学费。当时我哭了三天，但后来越来越喜欢教师这个行业。
 **学生**：老师，你大学是怎么保持专业排名第一的？
-**教师**：每天5点起床坚持学习，大学四年保持本专业41人中排名第一；自律和坚持是核心，同时积极参加比赛、加入学生会锻炼综合能力，评优不只看成绩。
+**教师**：专业共41人，我大学四年保持第一。靠的是每天5点起床坚持学习，自律和坚持是关键。成绩优异不只靠学习，还要参加各种比赛和活动，评优是多方面综合的。
+**学生**：老师，如果考不进年级前50怎么办？
+**教师**：可以先把梦想调整为考进年级前百，考进前百后再定前50的目标，一步步往前进。梦想需要量力而行，实现不了就调整目标，通过努力坚持去实现。
 # 课后任务与学习建议
 ## 课堂练习
-- **梦想条件讨论**：以航模爱好者何宗发（音）和想当歌手的普通人为观察对象，全班分4个大组组成“梦想观察团”，讨论实现梦想需要具备的条件，结论为坚持、努力、勇敢、机会、兴趣、能力和学习。
-- **梦想清单书写**：学生拿出纸写下自己的梦想，可仿照老师示例列清单，逐条写清梦想内容、预计实现时间及实现后的收获，写完后由每个小组第1个同学收集交给老师。
+- **梦想条件讨论**：以航模爱好者何宗发和普通歌手追梦视频为观察对象，分组讨论实现梦想所需条件，学生提出坚持、努力、天赋、勇敢、机会等，老师补充兴趣、能力与学习。
+- **梦想清单书写**：学生拿出纸写下自己的梦想清单，内容包括梦想内容、预计实现时间、实现后的收获，完成后由每组第1位同学收集上交。
 ## 复习重点
-- **实现梦想的三大必要条件**：学习、坚持、行动，三者缺一不可；具备全部条件时梦想会更快实现。
-- **梦想可分阶段调整**：目标实现不了时可先调整为更易达成的阶段目标（如先考进年级前百再冲前50），一步步向前推进。
-- **每个梦想都值得尊重**：不被嘲笑的梦想不是梦想；不要嘲笑任何人的梦想，无论其当前状态如何。
-- **机会留给有准备的人**：实现梦想需要机会，但机会永远留给有准备的人，需以兴趣、能力和学习作支撑。
+- **实现梦想三要素**：学习、坚持、行动是梦想实现必不可少的三个条件，三者兼备可加速梦想实现。
+- **梦想条件非绝对**：缺少某一条件梦想仍可能实现，但具备全部条件会更快达成目标。
+- **机会与准备**：机会永远留给有准备的人，需通过日常学习与行动积累实力。
+- **梦想可调整**：目标实现不了时可量力而行、分步调整，如先定年级前百再冲刺前50，逐步靠近大目标。
+- **梦想需尊重**：每一个梦想都值得尊重，不应嘲笑他人梦想，唱歌走调可通过后天学习调整。
 ## 学习建议
-- **制定梦想清单**：仿照老师示例，将梦想分条列出（如考上理想学校、加入学生会、考取教师资格证等），实现一项打一个勾，并标注预计用时与收获。
-- **分阶段设定目标**：先定小目标再定大目标，梦想可以一步步立高（如航模爱好者从国内舞台走向世界锦标赛），量力而行并及时调整。
-- **勇敢行动**：像班会中主动上台唱歌的同学一样，即使被起哄也要勇敢站上讲台展示自己，用行动推动梦想实现。
-- **坚持与自律**：老师为保持专业排名第一坚持每天5点起床，说明实现梦想需长期坚持与自律，可借鉴此做法规划日常学习节奏。</t>
+- **制定梦想清单**：仿照老师做法，将梦想分条列出（如考学、获奖、职业目标），实现一项打勾，并标注预计用时与收获。
+- **分步设定目标**：先定小目标再定大目标，如先考进年级前百再冲刺前50，逐级提升实现几率。
+- **坚持与行动**：以老师大学四年保持专业排名第一（专业共41人）为例，坚持每天5点起床等自律行动，将梦想落实到日常。
+- **勇敢尝试**：像班会中勇敢站上讲台唱歌的同学一样，抓住机会展示自己，不惧他人起哄与嘲笑。
+- **主动参与活动**：参考老师大学经历，积极参加学生会、社团、校运会等比赛，多方面锻炼自己、认识优秀的人。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>47.7</v>
+        <v>52.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9362/3129</t>
+          <t>9362/3305</t>
         </is>
       </c>
     </row>
@@ -4051,104 +4074,108 @@
       <c r="C11" t="inlineStr">
         <is>
           <t># 全文摘要
-本期新闻联播由央视播音员播报，围绕国内发展成就与国际动态展开，涵盖文化自信与改革、赵乐际访俄、夏粮丰收、铁路货运、快递业、油气管网、防汛及国内联播快讯等主题。文化方面，习近平总书记提出将中华优秀传统文化精华与马克思主义立场观点方法相结合，2023年10月首次提出习近平文化思想；赵乐际于7月9日至13日访俄并出席中俄议会合作委员会第九次会议，双方同意从立法机构层面落实两国元首共识。国内经济数据方面发布了夏粮、货运、快递等多组创新高数据，其中夏粮产量达2996亿斤、6月铁路发送货物3.32亿吨、上半年快递业务量超800亿件；防汛方面，重庆等地出现暴雨，水利部联合调度水库应对三峡洪峰。国际方面，特朗普竞选集会遭未遂刺杀，以军空袭加沙致90人死亡。本期以信息发布为主，未形成明确结论。
+本期新闻联播围绕国内发展成就与国际动态展开播报。国内方面，头条聚焦文化自信与中华民族现代文明建设，系统回顾党的十八大以来文化体制改革历史性成就，包括习近平总书记提出将中华优秀传统文化精华与马克思主义立场观点方法相结合，2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想，以及《深化文化体制改革实施方案》《关于实施中华优秀传统文化传承发展工程的意见》等标志性文件。赵乐际于7月9日至13日对俄罗斯进行正式友好访问，会见总统普京，与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议。国内经济数据方面发布了夏粮、铁路货运、快递、油气管网等多组创新高数据；渝川皖等地积极应对降雨天气，水利部部署防汛。国际方面，多国人士高度评价中国全面深化改革扩大开放成就，并报道特朗普遭未遂刺杀、以军空袭加沙致90人死亡、俄乌冲突、加拿大林火等事件。关键数字：夏粮产量2996亿斤创历史新高；6月国家铁路发送货物3.32亿吨，同比增长6.1%；上半年快递业务量超800亿件；预计全年新增油气管道里程超4000公里；北京上半年320个重大项目全部开工，总投资超4000亿元。
 # 分段速览
 ## 00:00-08:31 文化自信与中华民族现代文明建设
-习近平总书记强调将中华优秀传统文化精华与马克思主义立场观点方法相结合，在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时提出系列重要论述。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述“两个结合”重大意义；2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。文化体制改革方面，《深化文化体制改革实施方案》是中央深改领导小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。文化领域供给侧结构性改革深入推进，文化旅游深度融合、非遗保护传承制度完善、公共文化服务体系健全，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”。
-## 08:31-12:31 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
-全国人大常委会委员长赵乐际应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。在圣彼得堡会见总统普京，转达习近平主席的亲切问候，强调今年是中俄建交75周年，两国新时代全面战略协作伙伴关系高水平、高质量发展；在莫斯科与马特维延科、沃洛金分别会谈，表示要以两国元首重要共识为指引，深化多层级、多领域、多渠道交流合作。10日出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作五点建议。访问期间向俄无名烈士墓敬献花圈。
-## 12:39-14:21 夏粮产量创历史新高
-今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，夏粮首战告捷为全年粮食丰收奠定坚实基础。
+习近平总书记以文化自觉与历史担当，在“五位一体”总体布局中对文化建设作出战略部署，纵深推进文化体制改革，引领社会主义文化强国建设取得历史性成就。总书记在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时，强调要善于从中华优秀传统文化中汲取治国理政理念和思维，提出“我们五千年的文明，我们要尊重，也要弘扬，把它里边精华的东西和我们现在所坚持的马克思主义立场、观点、方法结合起来”。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述“两个结合”重大意义；2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。《深化文化体制改革实施方案》是中央深改领导小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。文化领域供给侧结构性改革深入推进，文化旅游深度融合、非遗保护传承制度日益完善，中华文明探源工程、国家文化公园建设、《复兴文库》等重大工程持续推进。我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。中华文化正跨越时空，为世界文明发展进步带来深刻启迪。
+## 08:31-12:39 赵乐际对俄罗斯进行正式友好访问
+应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。赵乐际向普京转达习近平主席的亲切问候，表示今年是中俄建交75周年，在两国元首战略引领下，中俄新时代全面战略协作伙伴关系高水平、高质量发展，中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识。普京表示俄中立法机构始终保持高水平合作，有助于在立法层面推进双边合作的优先议题。与马特维延科、沃洛金会谈时，赵乐际强调要以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持。马特维延科表示发展对华关系得到俄社会广泛认同和支持；沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。10日，赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作五点建议。访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
+## 12:39-14:21 我国夏粮产量创历史新高
+今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤，单产恢复性增长是夏粮产量增加的主要原因。为大面积提高单产，中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。小麦质量为近年来最好水平，由于集成技术推广应用、科学防灾减灾、收割晾晒及时，主产区一、二等小麦占比普遍较高。夏粮首战告捷为全年粮食丰收奠定坚实基础。
 ## 14:21-16:03 6月份国家铁路货运多项指标稳定增长
-国铁集团数据显示，6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，均创历史同期新高，我国铁路货运量、货运周转量等指标稳居世界首位。重点物资运输保障有力，化肥农药运量同比增长26.2%增幅最大，煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。境内运输网络更加完善，多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口。国际联运量质齐升，中欧班列6月累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
+国铁集团数据显示，6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高，我国铁路货运量、货运周转量等指标稳居世界首位。重点物资运输保障有力，化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量等均创历史同期新高。境内运输网络更加完善，连接内陆物流节点城市的多式联运快车已覆盖各省会城市，连接港口和内陆腹地城市的铁海快线班列已覆盖全国主要港口。国际联运量质齐升，6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%，有力保障了国际供应链产业链稳定畅通。
 ## 16:03-17:22 上半年我国快递业发展提速
-截至6月30日，今年我国快递业务量已达800亿件。快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，国际运输能力稳步增强；多地启用、升级跨境仓，农村寄递网络覆盖范围逐渐扩大。每天超1亿多件快递包裹在农村地区流动，5—6月生鲜商品进入销售旺季、电商促销拉动线上消费，快递日均业务量近5亿件。快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
+今年上半年我国快递业务量超800亿件，行业发展提速，动能不断释放。快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，国际运输能力稳步增强。在多地启用、升级跨境仓同时，农村寄递网络覆盖范围逐渐扩大，每天超1亿多件快递包裹在农村地区流动，特别是5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。截至6月30日，今年我国快递业务量已达800亿件。快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
 ## 17:22-19:12 我国油气管网建设提速“全国一张网”不断完善
-今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。到2025年将初步形成东北、西北、西南及海上四大油气战略通道，建成“五纵五横”天然气干线管网。
+今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程也正在加速推进。目前，我国主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。按照规划，到2025年我国将初步形成东北、西北、西南以及海上四大油气战略通道，同时建成“五纵五横”的天然气干线管网，进一步提升油气供应保障能力。
 ## 19:12-20:40 渝川皖等地积极应对降雨天气
-重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江部分地区出现内涝、滑坡等险情，消防救援人员转移被困群众；安徽滁州市全椒县加强巡堤，及时处置堤防渗漏和管涌。水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+从7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝，全力保障道路畅通。四川暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。强降雨导致安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防发生的渗漏和管涌等情况。水利部针对“七下八上”防汛关键期即将到来和雨情水情形势逐流域安排防御。目前长江1号、2号洪水正在演进，三峡水库15日将再迎来一次洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
 ## 20:40-23:38 国内联播快讯
-北京上半年320个市区重大项目全部开工，总投资超4000亿元，聚焦现代化产业、基础设施、城市更新等领域。燕矶长江大桥北岸主塔封顶，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军。内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底。外交部、全国妇联主办的“中非儿童手拉手”活动在中国儿童中心启动，纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。
-## 23:38-28:37 国际新闻
-多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放为世界提供更广阔的市场和发展机遇。美国前总统特朗普在宾夕法尼亚州巴特勒市竞选集会上遭未遂刺杀，右耳中枪受伤，一名观众死亡、两名受重伤，枪手为20岁左右宾夕法尼亚州男性，被特勤局狙击手打死，联邦调查局正展开调查。以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，内塔尼亚胡称目标是哈马斯下属武装派别领导人，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等也予以谴责。以军还袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地；叙利亚首都大马士革遭空袭致1名政府军士兵死亡、3人受伤。
-## 28:37-30:27 国际联播快讯与专题
-俄罗斯国防部称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向乌军军用火车停车点，摧毁20件装备；乌克兰武装部队总参谋部称击退俄军17次进攻。加拿大东北部纽芬兰与拉布拉多省林火蔓延，过火面积100平方公里，拉布拉多城9600人被疏散，全国正应对500多起活跃林火、超400起失控。《全面深化改革中国式现代化万千气象》专题聚焦上海、浙江坚定不移全面深化改革、扩大开放，在推进中国式现代化建设中走在前列。
+北京上半年320个市区重大项目全部开工，项目包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超过4000亿元。燕矶长江大桥北岸主塔封顶，下一步将转入主缆施工阶段，大桥连接湖北鄂州和黄冈，主跨1860米，上层设计为高速公路，下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。第二十三届环青海湖国际公路自行车赛在海北州门源县落下帷幕，经过8天8个赛段，来自国内外22支车队的154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。内蒙古第34届草原那达慕在锡林浩特市开幕，以“相约草原遇见那达慕”为主题，持续到8月底，其间开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。“中非儿童手拉手”活动在中国儿童中心启动，由外交部、全国妇联主办，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问，与中国儿童联谊联欢。
+## 23:38-24:29 多国人士高度评价中国全面深化改革扩大开放
+多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量。多国人士表示，中国推进深层次改革和高水平开放，不仅为中国打开发展空间，让中国人民过上更美好的生活，也为世界提供更广阔的市场和发展机遇。
+## 24:29-25:50 特朗普竞选集会遭未遂刺杀
+13日，在美国宾夕法尼亚州巴特勒市举行的美国前总统、共和党人特朗普竞选集会上发生枪击。特朗普在社交媒体上称其右耳中枪受伤，特朗普竞选团队当天称特朗普“状况良好”。枪击造成一名观众死亡，两名观众受重伤。美国特勤局通报称，事发时一名枪手从集会现场外高处向特朗普所在的演讲台“开了数枪”，枪手所处屋顶距离特朗普演讲台大约在180多米到270多米之间，枪手开枪后被特勤局狙击手打死。美联邦调查局称特朗普遭未遂刺杀，正对事件展开调查，枪手是一名20岁左右男性，来自宾夕法尼亚州，具体作案动机还有待查明。
+## 25:50-28:37 以军空袭加沙地带及黎巴嫩、叙利亚局势
+根据巴勒斯坦加沙地带卫生部门数据，以军13日对加沙地带南部汗尤尼斯马瓦西地区发动空袭，死亡人数升至90人，另有约300人受伤，死伤者中包括许多妇女和儿童。以色列总理内塔尼亚胡13日晚称，以军空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马，以色列今后将继续发动类似袭击。哈马斯方面表示以军袭击使局势“严重升级”。巴勒斯坦总统阿巴斯当天发表声明谴责以军违反国际法，约旦、卡塔尔、埃及等也发表声明予以谴责。以军13日还在加沙地带南部拉法、北部加沙城等地打击巴武装人员和军用设施，巴武装派别同一天称在拉法、加沙城等地使用迫击炮、火箭弹等打击以军阵地和坦克等目标。另据黎巴嫩媒体13日报道，黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因以军白磷弹袭击发生火灾，黎巴嫩真主党武装当天称打击了位于以色列北部的以军集结地及情报设施。叙利亚军方14日称，当天凌晨大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤，以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
+## 28:37-30:07 国际联播快讯
+俄罗斯国防部13日称，俄军使用“伊斯坎德尔-M”导弹打击了哈尔科夫方向一处乌军军用火车停车点，摧毁了包括3辆德制步兵战车在内的20件乌军装备。同一天，乌克兰武装部队总参谋部称，乌军在前线地区与俄军交战上百次，其中在波克罗夫斯克方向击退俄军17次进攻。加拿大东北部纽芬兰与拉布拉多省的林火迅速蔓延，目前过火面积达到100平方公里，拉布拉多城9600人被疏散，消防人员称随着火势迅速升级已无法继续使用灭火飞机，加拿大目前正在应对500多起活跃林火，其中超400起处于失控状态。
+## 30:07-30:27 全面深化改革中国式现代化万千气象
+新时代新征程，上海、浙江坚定不移全面深化改革、扩大开放，在推进中国式现代化建设中走在前列。本期《全面深化改革中国式现代化万千气象》走进上海、浙江。
 # 要点梳理
 ## 文化自信与中华民族现代文明建设
-- **理论创新**：习近平总书记提出把中华优秀传统文化精华与马克思主义立场、观点、方法相结合，为建设社会主义文化强国指明方向
-- **考察足迹**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院凝望“实事求是”匾额，指出一定要把真理本土化；在三苏祠强调善于从中华优秀传统文化中汲取治国理政的理念和思维；在武夷山朱熹园提出以时代精神激活中华优秀传统文化的生命力
-- **重要会议**：2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述“两个结合”尤其是“第二个结合”的重大意义；2023年10月全国宣传思想文化工作会议首次提出习近平文化思想
-- **制度文件**：《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署
-- **文化成就**：我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高；深入实施中华文明探源工程，高标准推进国家文化公园建设，中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版
-## 赵乐际访问俄罗斯
-- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议
-- **会见普京**：赵乐际转达习近平主席亲切问候，表示今年是中俄建交75周年，在两国元首战略引领下中俄新时代全面战略协作伙伴关系高水平、高质量发展；中国全国人大愿从立法机构层面落实两国元首重要共识
-- **普京表态**：请赵乐际转达对习近平主席的亲切问候，称俄中立法机构始终保持高水平合作，加强议会合作委员会工作有利于两国交流经验、互学互鉴，促进立法、地方等各领域合作
-- **与马特维延科、沃洛金会谈**：赵乐际提出以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持；用好中俄议会合作委员会、双边友好小组等机制和平台，互学互鉴立法经验
-- **俄方表态**：马特维延科表示发展对华关系得到俄社会广泛认同和支持，要加强立法合作，推进地方立法机构、青年议员和人大代表交流；沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政
-- **议会合作委员会第九次会议**：赵乐际10日出席并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作团结壮大“全球南方”力量等五点建议
-- **其他行程**：访问期间赵乐际在莫斯科向俄无名烈士墓敬献花圈
+- **理论指引**：习近平总书记提出将中华优秀传统文化精华与马克思主义立场、观点、方法相结合，强调“我们五千年的文明，我们要尊重，也要弘扬”。
+- **考察足迹**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院凝望“实事求是”匾额，指出一定要把真理本土化；在三苏祠强调汲取治国理政理念和思维；在武夷山朱熹园提出以时代精神激活中华优秀传统文化生命力。
+- **2023年6月**：习近平总书记主持召开文化传承发展座谈会，系统论述中华文明五个突出特性，阐述“两个结合”尤其是“第二个结合”的重大意义。
+- **2023年10月**：全国宣传思想文化工作会议首次提出习近平文化思想。
+- **标志性文件**：《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署。
+- **文化事业成就**：深入实施中华文明探源工程，高标准推进国家文化公园建设；中国共产党历史展览馆、国家版本馆等文化地标落成；《复兴文库》、“中国历代绘画大系”出版。
+- **产业成就**：我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
+## 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
+- **访问安排**：应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日对俄罗斯进行正式友好访问；在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。
+- **赵乐际表态**：今年是中俄建交75周年，在两国元首战略引领下，中俄新时代全面战略协作伙伴关系高水平、高质量发展；中国全国人大愿同俄罗斯联邦会议从立法机构层面落实两国元首重要共识。
+- **普京表态**：俄中立法机构始终保持高水平合作，有助于在立法层面推进双边合作优先议题；加强俄中议会合作委员会工作有利于两国交流经验、互学互鉴，促进立法、地方等各领域合作。
+- **与马特维延科、沃洛金会谈**：赵乐际提出以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持；用好中俄议会合作委员会、双边友好小组等机制和平台，互学互鉴立法经验。
+- **马特维延科表态**：发展对华关系得到俄社会广泛认同和支持；两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流。
+- **沃洛金表态**：俄国家杜马不同党派在发展对华关系上高度一致；俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
+- **中俄议会合作委员会第九次会议致辞（7月10日）**：赵乐际提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作团结壮大“全球南方”力量五点建议。
+- **其他行程**：赵乐际在莫斯科向俄无名烈士墓敬献花圈。
 ## 夏粮产量创历史新高
-- **总产量**：今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，克服多重自然灾害影响
-- **单产数据**：夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤；单产恢复性增长是产量增加的主要原因
-- **政策支撑**：中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金
-- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，得益于集成技术推广应用、科学防灾减灾、收割晾晒及时
-## 6月份国家铁路货运
-- **总体数据**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位
-- **重点物资**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高
-- **境内网络**：连接内陆物流节点城市的多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口
-- **国际联运**：6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%
-## 上半年快递业
-- **业务总量**：截至6月30日，今年我国快递业务量已达800亿件
-- **国际能力**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；多地启用、升级跨境仓
-- **农村网络**：每天超1亿多件快递包裹在农村地区流动，5—6月生鲜商品进入销售旺季、电商促销拉动线上消费，快递日均业务量近5亿件
-- **融合发展**：快递业不断丰富服务场景，拓展服务领域，实现与制造业融合发展
-## 油气管网建设
-- **总体目标**：预计全年新增管道里程超4000公里，“全国一张网”不断完善
-- **重点工程**：西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进
-- **管网能力**：主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米
-- **2025年规划**：初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网
-## 渝川皖等地应对降雨
-- **重庆**：7月13日8时至14日8时，九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨；组织工作人员连夜抢险排涝，保障道路畅通
-- **四川**：暴雨造成内江部分地区内涝、滑坡等险情，消防救援人员紧急出动转移被困群众
-- **安徽**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌
-- **水利部调度**：针对“七下八上”防汛关键期逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程；联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量
+- **总产量**：今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。
+- **单产**：夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤；单产恢复性增长是夏粮产量增加的主要原因。
+- **政策支撑**：中央深入推进“藏粮于地、藏粮于技”战略；全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金。
+- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高。
+## 6月份国家铁路货运多项指标稳定增长
+- **总体数据**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
+- **重点物资**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高。
+- **境内网络**：连接内陆物流节点城市的多式联运快车已覆盖各省会城市；连接港口和内陆腹地城市的铁海快线班列已覆盖全国主要港口。
+- **国际联运**：6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
+## 上半年我国快递业发展提速
+- **业务总量**：截至6月30日，今年我国快递业务量已达800亿件。
+- **国际网络**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线。
+- **农村网络**：每天超1亿多件快递包裹在农村地区流动；5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。
+- **融合发展**：快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
+## 我国油气管网建设提速
+- **总体进展**：预计全年新增管道里程超4000公里，“全国一张网”不断完善。
+- **重点工程**：西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
+- **输气能力**：我国主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%；天然气“全国一张网”日供气能力超10亿立方米。
+- **2025年规划**：初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”的天然气干线管网。
+## 渝川皖等地积极应对降雨天气
+- **重庆**：7月13日8时至14日8时，九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨；当地组织工作人员连夜抢险排涝，保障道路畅通。
+- **四川**：暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动，转移被困群众。
+- **安徽**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌。
+- **水利部部署**：针对“七下八上”防汛关键期即将到来和雨情水情形势逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程；联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
 ## 国内联播快讯
-- **北京重大项目**：上半年计划新开工的320个市区重大项目全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超4000亿元
-- **燕矶长江大桥**：7月14日北岸主塔封顶，下一步转入主缆施工阶段；连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道
-- **环青海湖国际公路自行车赛**：第二十三届7月14日在海北州门源县落幕，8天8个赛段，国内外22支车队154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军
-- **草原那达慕**：内蒙古第34届7月14日在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动
-- **中非儿童手拉手**：7月14日由外交部、全国妇联主办，在中国儿童中心启动；纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问
+- **北京重大项目**：上半年计划新开工的320个市区重大项目已全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超过4000亿元。
+- **燕矶长江大桥**：7月14日北岸主塔封顶，下一步转入主缆施工阶段；大桥连接湖北鄂州和黄冈，主跨1860米，上层为高速公路，下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
+- **环青海湖国际公路自行车赛**：第二十三届7月14日在海北州门源县收官，8天8个赛段，国内外22支车队154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
+- **内蒙古草原那达慕**：第34届7月14日在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
+- **“中非儿童手拉手”活动**：7月14日由外交部、全国妇联主办，在中国儿童中心启动；来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问。
 ## 国际新闻
-- **多国人士评价**：高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放在许多领域实现历史性变革，为世界提供更广阔的市场和发展机遇
-- **特朗普竞选集会枪击**：13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击，特朗普在社交媒体称右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众受重伤；枪手从集会现场外高处向演讲台“开了数枪”，所处屋顶距演讲台约180多米到270多米，开枪后被特勤局狙击手打死；美联邦调查局称特朗普遭未遂刺杀，枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明
-- **以军空袭加沙马瓦西地区**：13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者中包括许多妇女和儿童；内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马，今后将继续发动类似袭击；哈马斯表示袭击使局势“严重升级”
-- **各方谴责**：巴勒斯坦总统阿巴斯发表声明谴责以军违反国际法；约旦、卡塔尔、埃及等发表声明予以谴责
-- **加沙其他冲突**：以军13日在拉法、加沙城等地打击巴武装人员和军用设施；巴武装派别使用迫击炮、火箭弹等打击以军阵地和坦克
-- **以黎冲突**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾；黎真主党武装称打击了位于以色列北部的以军集结地和情报设施
-- **叙利亚遭空袭**：叙利亚军方7月14日称大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标
-- **俄乌冲突**：俄国防部称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌武装部队总参谋部称当天与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻
-- **加拿大林火**：13日纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大正应对500多起活跃林火，其中超400起处于失控状态
+- **多国人士评价**：高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量。
+- **特朗普竞选集会枪击**：7月13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击，特朗普称右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众重伤；枪手从集会现场外高处向演讲台开枪，所处屋顶距演讲台约180多米到270多米，开枪后被特勤局狙击手打死；美联邦调查局称特朗普遭未遂刺杀，枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明。
+- **以军空袭加沙马瓦西地区**：7月13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人，约300人受伤，死伤者中包括许多妇女和儿童；以色列总理内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马，今后将继续发动类似袭击；哈马斯表示袭击使局势“严重升级”。
+- **巴勒斯坦及多国谴责**：巴勒斯坦总统阿巴斯发表声明谴责以军违反国际法；约旦、卡塔尔、埃及等发表声明予以谴责。
+- **加沙其他冲突**：以军13日在拉法、加沙城等地打击巴武装人员和军用设施；巴武装派别使用迫击炮、火箭弹等打击以军阵地和坦克。
+- **黎以冲突**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾；黎巴嫩真主党武装打击了位于以色列北部的以军集结地和情报设施。
+- **叙利亚遭空袭**：叙利亚军方7月14日称，大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
+- **俄乌冲突**：俄国防部13日称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌武装部队总参谋部称当天在前线地区与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
+- **加拿大林火**：13日纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大目前应对500多起活跃林火，其中超400起处于失控状态。
 ## 结论与决定
-- **文化领域**：全党全国各族人民文化自信明显增强，全社会凝聚力和向心力极大提升；文化体制改革在正本清源、守正创新中取得历史性成就、发生历史性变革
-- **中俄关系**：双方同意从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作；俄方明确坚定恪守一个中国原则
-- **夏粮生产**：夏粮首战告捷，为全年粮食丰收奠定坚实基础
-- **铁路货运**：6月份多项指标创历史同期新高，铁路货运量、货运周转量等指标稳居世界首位
+- **文化体制改革**：党的十八大以来，文化体制改革在正本清源、守正创新中取得历史性成就，全党全国各族人民文化自信明显增强，全社会凝聚力和向心力极大提升。
+- **中俄关系**：中俄立法机构将深化多层级、多领域、多渠道交流合作，从立法机构层面落实两国元首重要共识；沃洛金明确俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
+- **夏粮生产**：夏粮首战告捷，为全年粮食丰收奠定坚实基础。
 ## 行动项与分工
-- **水利部**：针对“七下八上”防汛关键期逐流域安排防御，联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量
-- **美联邦调查局**：对特朗普竞选集会枪击事件展开调查，枪手具体作案动机有待查明
-## 待确认与风险
-- **特朗普枪击案**：枪手为20岁左右男性、来自宾夕法尼亚州，具体作案动机还有待查明
-- **以军空袭**：内塔尼亚胡称今后将继续发动类似袭击，哈马斯表示袭击使局势“严重升级”
-- **加拿大林火**：火势迅速升级，已无法继续使用灭火飞机，超400起活跃林火处于失控状态</t>
+- **水利部**：针对“七下八上”防汛关键期逐流域安排防御，联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+- **美联邦调查局**：对特朗普遭未遂刺杀事件展开调查，枪手具体作案动机有待查明。</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>75.7</v>
+        <v>82.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7755/7574</t>
+          <t>7755/9268</t>
         </is>
       </c>
     </row>
@@ -4387,142 +4414,118 @@
       <c r="C12" t="inlineStr">
         <is>
           <t># 课程概况
-本课为初中物理光学复习课，系统复习几何光学核心知识，涵盖光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用。主讲人指出几何光学自古希腊时期即有研究，初中阶段主要学习直线传播、反射与折射规律。光的直线传播部分讲解光源（自然光源与人造光源）、光线（物理模型）概念，通过激光笔与烟雾实验、吸管弯折实验证明光在均匀介质中沿直线传播，并指出大气层不均匀会导致光线偏折；实例包括三点一线瞄准、激光准直、小孔成像、日食月食、影子形成，光在真空中速度为3×10⁸米/秒。光的反射定律强调三线共面、分居两侧、反射角等于入射角，法线为垂直镜面的辅助线，光垂直入射时入射角与反射角均为0度。镜面反射与漫反射对比中，黑板反光属镜面反射，电影银幕产生漫反射，雨后夜晚判断水潭位置及光路可逆性均有涉及。平面镜成像特点为正立、等大、虚像，实验用玻璃板代替平面镜便于确定像的位置，并讨论实验误差原因。球面镜部分介绍凸面镜发散光线、凹面镜会聚光线及其应用，并提及玻璃幕墙光污染隐患。
+本课为初中物理光学复习课，系统复习光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用。主讲人从光源定义（自身能发光的物体，分自然光源如太阳、人造光源如火把、电灯）和光线概念（带箭头的直线，是物理模型）入手，讲解光在均匀介质中沿直线传播，并通过三点一线、激光准直、小孔成像、日食月食、影子形成等实例加以说明。光在真空中的传播速度为3×10⁸米/秒（约30万公里/秒），一秒钟绕地球赤道7圈半；空气中略小于真空，水中约为真空的3/4，玻璃中约为真空的2/3。例题计算：激光从地球射到月球表面时间1.25秒，距离为3.75×10⁸米。光的反射定律为三线共面、分居两侧、反射角等于入射角，垂直入射时入射角和反射角均为0度；镜面反射易造成反光，漫反射是生活中大多数反射。平面镜成像特点为正立、等大、虚像，实验用玻璃板代替平面镜便于确定像的位置。球面镜方面，凸面镜发散光线用于汽车后视镜，凹面镜会聚光线用于手电筒、太阳灶等。
 # 核心知识点梳理
 ## 光的直线传播
-- **光源定义**：自身能够发光的物体，分为**自然光源**（如太阳）和**人造光源**（如火把、蜡烛、煤油灯、电灯）。
-- **光线概念**：用一条带有箭头的直线代表光线，是**物理模型**，并非真实存在；按来源分为自然光源与人造光源，按形状分为点光源（如蜡烛）与平行光源（如太阳从无限远处来，画成一束平行光）。
-- **光沿直线传播条件**：光在**均匀介质**中沿直线传播；大气层不均匀时会发生偏折，如太阳越出地平线、夜晚星星眨眼。
-- **证明实验**：玻璃罩内用激光笔照射，借助熏香或烟雾显示光路；用吸管做实验——吸管弯折后，激光在墙上光点消失，说明光不会自行拐弯。
-- **实例——三点一线**：步枪瞄准时眼睛、准心尖、标尺缺口三者重合，依据是光在均匀介质中沿直线传播；队列排齐、木工师傅闭一只眼看尺子是否平直同理。
-- **实例——激光准直**：利用激光沿直线传播的特性进行准直。
-- **实例——小孔成像**：光沿直线传播，成**倒立实像**，放大缩小不一定，与孔形状无关；《墨经》有记载，考试常考。
-- **小孔成像生活案例**：夏天大杨树下地面上的光斑，是太阳透过树叶缝隙形成的小孔成像，因太阳距地球远大于缝隙距地面距离，得到的是**缩小的实像**，角度不正时呈椭圆形。
-- **小孔成像自制实验**：纸杯底部用针扎小孔，杯口蒙塑料布，点燃蜡烛放在孔前，可在塑料布上看到**倒立的火苗像**。
-- **实例——日食**：太阳、月球、地球在同一直线上，**月球在中间**；1号区域为**日全食**，2、3号区域为**日偏食**，4号区域为**日环食**。
-- **实例——月食**：太阳、地球、月球在同一直线上，**地球在中间**；月球完全进入1号区域为**月全食**；月球部分在1号区域、部分在2或3号区域时出现**月偏食**（仅处于2、3号区域只会略暗，不叫月偏食）。
-- **实例——影子形成**：影子即俗称的阴影，唐朝皮影戏利用此原理。
-- **光速**：光在真空中的传播速度为 `3×10^8` 米/秒，即 `3×10^5` 千米/秒，约**每秒绕地球赤道7圈半**；空气中略慢，近似取 `3×10^8` 米/秒；水中约为真空中的 `3/4`，玻璃中约为 `2/3`。
-- **介质含义**：此处介质指**透明**物质（如有机玻璃、水），砖头、黑板不算；海水清澈时太阳光最多到达约**200米**深处。
-- **光速测量**：前人测量光速均失败，初三将学习光本质为电磁波，电磁波速度即 `3×10^8` 米/秒。
-- **练习1**：影子和月全食均依据光在均匀介质中沿直线传播。
-- **练习2**：激光从地球射到月球表面用时1.25秒，距离 `s=V×T`，地球与月球间视为真空，答案 `3.75×10^8` 米。
-- **练习3**：先看到闪电后听到雷声，因为**光速比声速快**（声速15℃时约340米/秒）。
-- **练习4**：选C——光在均匀介质中沿直线传播；D错在未强调均匀介质。
-- **练习5**：多选，选BCD——平面镜是反射现象。
-- **练习6**：选ABC；D错在光说传播路线，须强调均匀介质。
+- **光源定义**：自身能够发光的物体，分为**自然光源**（如太阳、萤火虫）和**人造光源**（如火把、蜡烛、煤油灯、电灯）。
+- **光线概念**：用一条带有箭头的直线代表光线，是**物理模型**，并非真实存在；按形状可分为点光源（如蜡烛）和平行光源（如太阳）。
+- **光沿直线传播条件**：在**均匀介质**中沿直线传播；大气层不均匀时会发生偏折，如太阳越出地平线、星星眨眼睛。
+- **三点一线实例**：步枪瞄准时眼睛、准心尖、标尺缺口三者重合，依据是光在均匀介质中沿直线传播；队列排齐、木工闭眼检查尺子是否平直同理。
+- **激光准直**：利用激光沿直线传播进行准直，是光沿直线传播的实例。
+- **小孔成像**：成**倒立实像**（光线实际到达），放大缩小不一定，与孔的形状无关；《墨经》有记载，是常考内容。
+- **小孔成像生活实例**：夏天大杨树下地面上的光斑是太阳透过树叶缝隙形成的小孔成像，因太阳距地球远大于树叶缝隙到地面距离，得到的是**缩小的实像**，角度不正时呈椭圆形。
+- **小孔成像自制实验**：纸杯底部用针扎小孔（不能用钉子扎大孔），前方用塑料布蒙上，点燃蜡烛放在孔前，可在塑料布上看到倒立的火苗像。
+- **日食形成**：太阳、月球、地球在同一直线上，**月球在中间**；1号区域为**日全食**，2、3号区域为**日偏食**，4号区域为**日环食**。
+- **月食形成**：太阳、地球、月球在同一直线上，**地球在中间**；月球完全进入1号区域为**月全食**，部分在1号区域、部分在2或3号区域时才出现**月偏食**（仅处于2、3号区域只会略暗，不叫月偏食）。
+- **影子形成**：影子（俗称阴影）的形成是光沿直线传播的实例，中国唐朝的皮影戏利用了这一原理。
+- **光速数值**：光在真空中的传播速度为 `3×10^8` 米/秒（即 `3×10^5` 千米/秒，约每秒30万公里），**一秒钟绕地球赤道7圈半**。
+- **光速在不同介质中**：空气中约为 `2.99×10^8` 米/秒，比真空中略慢（近似相等）；水中约为真空中的 **3/4**；玻璃中约为真空中的 **2/3**。
+- **光速例题**：激光从地球射到月球表面用时1.25秒，按 `s=V×T` 计算，地月距离为 `3.75×10^8` 米。
+- **闪电与雷声**：先看到闪电后听到雷声，因为**光速比声速快**（声速15℃时为340米/秒）；百米赛跑计时员若手掐表易出错，因人和机器反应速度有差异。
 ## 光的反射定律
-- **基本概念**：`AO` 为入射光线，`O` 为入射点，`OB` 为反射光线；`ON` 为**法线**，垂直于镜面，是入射光线与反射光线夹角的角平分线；入射光线与法线的夹角为**入射角**，反射光线与法线的夹角为**反射角**。
+- **基本概念**：入射光线AO射到平面镜上，O为入射点，反射光线为OB；**法线**是垂直于镜面的辅助线（不存在，画虚线），是入射角与反射角的角平分线；入射角是入射光线与法线的夹角，反射角是反射光线与法线的夹角。
 - **反射定律三句话**：①反射光线、入射光线、法线在**同一平面内**（共面）；②反射光线和入射光线**分居法线两侧**；③**反射角等于入射角**。
-- **法线引入原因**：为后续学习折射做准备，法线是辅助线，**不存在**，画图用虚线。
-- **易错点**：光垂直射到镜面上时，入射角和反射角均为**0度**（不是90度）。
-- **例题——第9题**：反射光线与平面镜夹角40度，则与法线夹角50度，入射角为**50度**，选A。
-- **作图步骤**：①先画法线（虚线，画两三段断开即可，作图痕迹保留）；②根据反射角等于入射角，用刻度尺在法线两侧找对称点（如一侧5厘米，另一侧找5厘米）；③连接入射点与对称点，补全箭头。
-- **作图易错**：箭头方向画反（两条光线各往各的方向飞或相对着画），此类题定位为送分题。
-- **练习10**：入射光线与镜面夹角增大，入射角减小，反射角也减小，传播速度不变，选C。
-- **练习11**：入射光线与法线夹角60度，反射角为**60度**。
-- **练习12**：反射光线与入射光线夹角80度，反射角为**40度**（角平分线）。
+- **垂直入射易错点** ⭐：光垂直射到镜面上时，入射角和反射角都是 **0度**（不是90度），因为入射角是入射光线与法线的夹角。
+- **夹角计算**：反射光线与平面镜夹角为40度时，与法线夹角为50度，故入射角为50度；反射光线与入射光线夹角为80度时，反射角为40度（角平分线）。
+- **作图方法步骤**：①先画法线（虚线，画两三段断开即可，不用画太密）；②根据反射角等于入射角，用尺子刻度对准法线，在两侧找对称点（如反射光上取距法线5厘米的点，入射侧找对称点）；③连接入射点与对称点画出光线，补全箭头；**作图痕迹保留法线**，不要求数学般精确。
+- **作图易错点**：箭头方向画反（两条光线各往各的方向飞或对着画）是常见错误；此类题定位为送分题。
 ## 镜面反射与漫反射
-- **镜面反射**：平行光射到光滑表面，各入射点法线均与镜面垂直，入射角相同，反射光平行射出；人眼只在特定位置能看到反射光，如商场玻璃隔断易使人撞上。
-- **漫反射**：表面凹凸不平，将每个小面看作小平面镜，平行光反射后射向**各个方向**，人眼在任何位置都能看到；生活中大多数反射是漫反射。
-- **黑板反光**：教室某些位置看黑板只见一片光亮、看不清粉笔字，是黑板发生**镜面反射**；电影银幕、投影幕布表面粗糙，发生**漫反射**。
-- **练习13（雨后水潭）**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭。
-- **自制实验**：白纸上放小镜子，手电筒垂直照射，斜着看时**镜子是黑的、白纸是亮的**——镜子发生镜面反射光返回，白纸发生漫反射。
-- **练习14（光路可逆）**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明，依据是**光路可逆**；A错（垂直入射反射角0度）、C错（漫反射也遵守反射定律）、D错（不同介质光速不同）。
-- **练习15**：电影院白色荧幕对光产生**漫反射**。
-- **练习16**：黑板反光为**镜面反射**，电影放映机射到银幕的光经幕布反射为**漫反射**，两种反射都遵守光的反射定律。
-- **练习17**：电影院白色屏幕粗糙，为使射到屏幕的光发生**漫反射**。
+- **镜面反射**：平行光射到光滑表面（如平面镜），各入射点法线平行，反射光平行射出；人眼不在反射光方向上就看不到反射光，如商场玻璃隔断易使人撞上。
+- **漫反射**：表面凹凸不平（放大镜下看再光滑的物体也凹凸不平），把每个小面看作小平面镜，平行光反射后射向**各个方向**；生活中大多数反射是漫反射，如黑板、人本身。
+- **共同点**：镜面反射和漫反射**都遵守光的反射定律**。
+- **黑板反光问题**：教室某些位置看黑板只见一片光亮而看不清粉笔字，是黑板发生**镜面反射**；电影院白色银幕粗糙，为使射到屏幕上的光发生**漫反射**。
+- **雨后水潭判断** ⭐：雨后夜晚，**迎着月光走**时发亮处是水潭（水面发生镜面反射）；**背着月光走**时发暗处是水潭。
+- **自制验证实验**：白纸上放一面小镜子，用手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的——镜子发生镜面反射光线返回，白纸表面粗糙发生漫反射。
+- **光路可逆**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明在平面镜中的像，依据是**光路可逆**。
 ## 平面镜成像
-- **成像原理**：根据光的反射定律作图，反射光线反向延长线的交点即像点 `S'`；像与物的连线**垂直于镜面**，像到镜面距离**等于**物到镜面距离。
-- **成像特点**：成**正立、等大、虚像**（与小孔成像的倒立实像不同）。
-- **实验器材与作用**：用**玻璃板**代替平面镜（便于移动后方蜡烛确定像的位置）；**刻度尺**用于比较像与物到镜面的距离；**两段完全相同蜡烛**用于比较像与物的大小。
-- **虚像验证**：光屏（毛玻璃、白塑料片、白墙等）**不能**接收到烛焰的像，因为实际光线没有到达镜后；后方蜡烛看似被点燃，手放上去不会被烫伤。
-- **实验误差原因一**：玻璃板与水平面**不垂直**（或与事先画好的镜面位置不重合），导致测量数据不相等。
-- **实验误差原因二**：玻璃板**有厚度**，两个面都发生反射成像；薄玻璃板（约3毫米）人眼分辨不出两个像，厚玻璃板（约8毫米）会看到同一个蜡烛的两个像。
-- **练习18**：人在河边看到岸边的树在水中的倒影属于光的反射（平静水面充当平面镜，成正立等大虚像，文学上称"倒影"）；C选项"看到河水深度比实际浅"是光的折射。
-- **练习21（查视力）**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子**1.5米**时看到虚像距离为5米。
-- **练习22**：视力表到镜距离改为3米，像到镜距离3米，人距镜子**2米**即可，选B。
-- **练习23**：人站在平面镜前1米处，人与像之间距离为**2米**。
-- **练习24**：人向远离平面镜方向移动，镜中像的大小**不变**，选C。
+- **成像原理**：根据光的反射定律作图，反射光线的反向延长线交于镜后一点，即为像点S′；像与物的连线**垂直镜面**，像到镜面距离等于物到镜面距离。
+- **成像特点**：成**正立、等大、虚像**（与小孔成像的倒立实像不同）；虚像处实际光线未到达，光屏不能接收到。
+- **实验器材选择**：用**玻璃板代替平面镜**，便于移动后方蜡烛确定像的位置；用**刻度尺**比较像与物到镜面的距离；用**两段完全相同的蜡烛**比较像与物的大小。
+- **光屏实验**：光屏可用毛玻璃、刷白漆的铁皮、白塑料板或白墙充当；光屏**不能**接收到蜡烛烛焰的像，因为虚像处实际光线没有到达。
+- **实验误差原因一**：玻璃板与水平面**不垂直**（或与事先画好的镜面位置不重合），导致像与物连线不垂直镜面、距离不相等。
+- **实验误差原因二**：玻璃板**有厚度**，两个面都会发生反射成像；薄玻璃板（如3毫米）人眼区分不开两个像，厚玻璃板（如8毫米）会看到同一个蜡烛的两个像。
+- **视力表例题**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子**1.5米**时看到虚像距离为5米；若视力表距镜子改为3米，人距镜子2米即可。
+- **人与像距离**：人站在平面镜前1米处，人与像之间的距离为2米；人向远离平面镜方向移动，镜中像的大小**不变**。
+- **水中倒影辨析** ⭐：人在河边看到岸边的树在水中的倒影属于光的反射（平静水面充当平面镜），成的是正立等大的虚像，只是文学上习惯称“倒影”，与折射现象不同；看到河水深度比实际浅是光的折射。
 ## 球面镜及其应用
-- **凸面镜**：对光线起**发散作用**，成正立、缩小的虚像；用于汽车后视镜、丁字路口拐弯处反光镜（能看到更大范围，但视觉上物体显得比实际远）。
-- **凹面镜**：对光线起**会聚作用**，平行光反射后汇聚于焦点 `F`；用于手电筒电珠（小灯泡置于焦点处）、汽车前大灯、探照灯、医生额镜（中间镂空便于观察耳道、鼻腔、嗓子）、西藏藏民使用的太阳灶。
-- **作图方法**：以直代曲——将曲面看作许多小平面镜，逐面画法线与反射光线。
-- **阿基米德案例**：组织妇女用梳妆平面镜围成凹面，汇聚光线烧毁敌人帆船。
-- **玻璃幕墙光污染**：玻璃幕墙做成凹面会汇聚光线，可能烧死树木（学校枣树三年被烧死）、引燃电线（焦点落在电线上导致自燃）；凹面还反射声音，楼间噪音增大。
+- **凸面镜**：对光线起**发散作用**，成**正立、缩小的虚像**；用于汽车后视镜、丁字路口拐弯处反光镜（能看到更大范围，但视觉上物体显得比实际远）。
+- **凹面镜**：对光线起**会聚作用**，平行光反射后汇聚于焦点F；用于手电筒电珠（小灯泡置于焦点处）、汽车前大灯、探照灯、医生额镜（中间镂空便于观察耳道、鼻腔、嗓子）、西藏藏民的太阳灶。
+- **以直代曲原则**：讨论球面镜作图时，把曲面看作许多小平面镜的组合，这是物理上的“以直代曲”方法。
+- **阿基米德传说**：曾组织妇女用梳妆镜（平面镜）围成凹面，汇聚光线烧毁敌人帆船。
+- **玻璃幕墙光污染** ⭐：玻璃幕墙做成凹面会汇聚光线，可能烧死树木（学校枣树三年被烧死）、引燃电线造成自燃，还会反射声音造成噪音，属于**光污染**隐患。
 # 课堂互动与答疑
 **学生**：为什么研究反射时要引入法线，直接用入射光线和镜面的夹角不行吗？
-**教师**：如果只研究反射，用镜面夹角确实可以，但后面还要学折射，折射定律需要以法线为基准来定义入射角和折射角，所以必须统一引入法线。法线是垂直于镜面的辅助线，也是入射光线和反射光线夹角的角平分线，实际并不存在，画图时用虚线表示。
-**学生**：光垂直射到镜面上，入射角和反射角是多少？为什么不是90度？
-**教师**：都是0度。因为入射角的定义是入射光线与法线的夹角，垂直入射时光线与法线重合，夹角为0度，反射角也等于0度。这是常见易错点，很多同学误答成90度。
-**学生**：画反射光线时，怎么确定入射光线的位置？需要用量角器量角度吗？
-**教师**：不需要量角器。作图步骤是：先画法线（虚线，留作图痕迹），再根据反射角等于入射角确定光线位置。简便方法是用刻度尺的刻度对准法线，在入射光线和反射光线方向上各找一个到法线距离相等的点，连接入射点即可，这样画出的两条光线一定对称。
-**学生**：为什么说小孔成像成的像一定是实像？放大缩小不一定？
-**教师**：因为光线实际到达光屏，所以是实像。像的大小取决于物距和像距的关系：物体离孔远、光屏离孔近时成缩小的像，反之成放大的像，但倒立是肯定的。像的形状与孔的形状无关，只与物体形状有关，如树叶缝隙形成的光斑是太阳的像。
-**学生**：日食和月食的偏食区域为什么不一样？月偏食不是月球在2、3号区域吗？
-**教师**：日食时月球在中间，2、3号区域是日偏食；但月食时地球在中间，月球很小，可以完全钻入地球阴影（1号区域）形成月全食。如果月球部分在1号区域、部分在2或3号区域，才出现月偏食；完全在2或3号区域时只是略暗，不叫月食。
-**学生**：光在真空中的速度是3×10⁸米/秒，那在其他介质中呢？
-**教师**：真空中是3×10⁸米/秒，空气中略慢，约为2.99×10⁸米/秒，通常近似取真空值；水中约为真空中的3/4，玻璃中约为2/3。光速随介质不同而变化，所以不能说光在所有介质中速度都相同。
-**学生**：为什么用玻璃板代替平面镜做成像实验？直接用镜子不行吗？
-**教师**：不行。平面镜不透光，无法看到镜后的蜡烛位置，也就无法确定像的位置。玻璃板既能反射成像，又能透过它看到后面的蜡烛，便于移动未点燃的蜡烛与像重合，从而确定像的位置并比较像与物的大小和距离。
-**学生**：实验中为什么能看到同一个蜡烛的两个像？
-**教师**：因为玻璃板有厚度，前后两个表面都能发生反射，各自成一个像。如果玻璃板很薄（如3毫米），两个像几乎重合，肉眼分辨不出；如果玻璃板较厚（如8毫米），就能明显看到两个像。所以实验应选薄玻璃板。
-**学生**：为什么光屏接收不到平面镜成的像？
-**教师**：因为平面镜成的是虚像，实际光线并没有到达镜后，只是人眼逆着反射光线的方向看过去，感觉像在镜后。所以把光屏放在像的位置，接收不到任何光线，也就看不到像。这与小孔成像不同，小孔成像是实际光线到达光屏形成的实像。
-**学生**：雨后夜晚，为什么迎着月光走时发亮处是水潭，背着月光走时发暗处是水潭？
-**教师**：水面发生镜面反射。迎着月光走时，月光经水面反射后恰好进入人眼，所以水潭发亮；背着月光走时，反射光射向另一侧，进入人眼的反射光很少，而地面发生漫反射，反而比水面亮，所以发暗处是水潭。
-**学生**：凸面镜和凹面镜对光线各起什么作用？分别用在哪些地方？
-**教师**：凸面镜对光线起发散作用，成**正立、缩小的虚像**，用于汽车后视镜、丁字路口反光镜，能扩大视野；凹面镜对光线起会聚作用，把平行光会聚到焦点，用于手电筒、汽车前大灯、太阳灶、医生额镜。凹面镜会聚光线也可能造成危害，如玻璃幕墙形成凹面会聚阳光，可能烧死树木甚至引燃电线。
+**教师**：引入法线是为了给后续光的折射做准备，折射定律需要以法线为基准来定义入射角和折射角。若只研究反射，用镜面夹角也可以，但光学体系要统一，所以必须用法线。
+**学生**：光垂直射到镜面上，入射角是多少？
+**教师**：入射角是入射光线与法线的夹角，垂直入射时二者重合，入射角为0度，反射角也为0度。这是常见易错点，不能答成90度。
+**学生**：平面镜成像实验中，为什么用玻璃板代替平面镜？
+**教师**：玻璃板既能反射成像又能透光，便于在另一侧移动蜡烛确定像的位置；若用不透明平面镜，无法看到后方蜡烛与像重合，实验无法完成。
+**学生**：为什么光屏上接收不到平面镜所成的像？
+**教师**：平面镜成的是虚像，反射光线的反向延长线会聚而成，实际光线并未到达像的位置，所以光屏接收不到。小孔成像则相反，实际光线到达光屏，成实像。
+**学生**：实验中看到同一个蜡烛有两个像，是什么原因？
+**教师**：玻璃板有厚度，前后两个表面都会发生反射成像。薄玻璃板两像几乎重合肉眼难辨，厚玻璃板（如8毫米）两像明显分离，所以实验应选薄玻璃板。
+**学生**：雨后夜晚，怎样判断哪里是水潭？
+**教师**：迎着月光走，水面发生镜面反射，反射光进入人眼，发亮处是水潭；背着月光走，反射光无法进入人眼，水面发暗，而地面漫反射光进入人眼相对更亮，所以发暗处是水潭。
+**学生**：凸面镜和凹面镜对光线的作用有什么不同？
+**教师**：凸面镜对光线起发散作用，成缩小正立虚像，用于汽车后视镜、丁字路口反光镜；凹面镜对光线起会聚作用，用于手电筒、汽车前大灯、太阳灶、医生额镜。
 # 课后任务与学习建议
 ## 课堂练习
-- **第1–5题（光的直线传播）**：考点为光在均匀介质中沿直线传播及光速计算。第1题答案即该原理；第2题影子和月全食均依据此原理；第3题激光从地球到月球用时1.25秒，按s=vt计算，地月距离为3.75×10⁸米；第4题选C，光在真空中传播速度最快，均匀介质中沿直线传播，不同介质中速度不同；第5题多选BCD，平面镜成像属反射而非直线传播。
-- **第6题（多选）**：考点为光沿直线传播的条件，选ABC；D项错在未强调均匀介质，光传播路线并非无条件为直线。
-- **第7题（反射定律探究实验）**：考点为光的反射定律验证。用带刻度硬纸板（中间用透明胶带粘合可前后转动）和小平面镜，激光笔照射，观察反射光线、入射光线与法线关系，验证三线共面、分居两侧、反射角等于入射角。
-- **第8题（反射作图）**：考点为根据反射定律画入射或反射光线。步骤：先画法线（虚线，2–3段即可），再根据反射角等于入射角确定光线方向，最后补全箭头；可用尺子刻度找对称点辅助作图，作图痕迹保留法线即可。
-- **第9题（选择题）**：考点为入射角与反射角计算。反射光线与平面镜夹角40°，则与法线夹角（入射角）为50°，反射角也为50°，选A。
-- **第10题（选择题）**：考点为入射角变化对反射角的影响。入射光线与镜面夹角增大时，入射角减小，反射角随之减小，但传播速度不变，选C。
-- **第11题**：入射光线与法线夹角60°时，反射角为60°。
-- **第12题**：反射光线与入射光线夹角80°时，反射角为40°（角平分线）。
-- **第13题（雨后水潭判断）**：考点为镜面反射与漫反射辨析。迎着月光走，发亮处是水潭（水面镜面反射）；背着月光走，发暗处是水潭；选B。
-- **第14题（光路可逆）**：A错，垂直入射时入射角为0°而非90°；B对，小明能看到小刚在平面镜中的像，则小刚也一定能看到小明（光路可逆）；C错，漫反射同样遵守反射定律；D错，光在不同介质中速度不同。
-- **第15题**：电影院白色荧幕对光产生漫反射，选B。
-- **第16题（填空）**：教室某些位置看黑板只见光亮看不清粉笔字，是黑板发生镜面反射；电影放映机射到银幕的光经幕布反射进入人眼，是漫反射；两种反射都遵守光的反射定律。
-- **第17题**：电影院白色屏幕粗糙，为使射到屏幕上的光发生漫反射。
-- **第18题（选择题）**：下列现象属于光的反射的是D——人在河边看到岸边树在水中的倒影（平静水面充当平面镜）；A、B属直线传播，C属折射。
-- **第19题（平面镜成像实验）**：考点为实验误差分析。①蜡烛到玻璃板距离与像到玻璃板距离不相等，原因可能是玻璃板与水平面不垂直（或与事先画好的镜面位置未重合）；②同一侧看到同一个蜡烛的两个像，原因是玻璃板有厚度，两个面发生反射成像。
-- **第20题（平面镜成像实验）**：①用玻璃板代替平面镜的目的是便于确定像的位置（可透过玻璃板移动后方蜡烛找像）；②刻度尺用于比较像与物到镜面的距离；③两段完全相同蜡烛用于比较像与物的大小；④光屏不能接收到烛焰的像，因为平面镜成虚像，实际光线未到达后方；⑤物体靠近玻璃板时，像的大小不变。
-- **第21题（填空）**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子1.5米时，看到虚像距离为5米，填1.5米。
-- **第22题（选择题）**：视力表到镜距离改为3米，像到镜距离也是3米，人距镜子2米即可，选B。
-- **第23题**：人站在平面镜前1米处，人与像之间距离为2米。
-- **第24题**：人向远离平面镜方向移动，镜中像的大小不变，选C。
+- **练习1–5（光的直线传播）**：第1题考查光在均匀介质中沿直线传播；影子和月全食均据此解释；第2题激光从地球射到月球表面用时1.25秒，按真空光速3×10⁸米/秒计算，距离为3.75×10⁸米；第3题先看到闪电后听到雷声，因光速比声速快（声速约340米/秒）；第4题选C，光在真空中传播速度最大；第5题多选BCD，平面镜成像属反射而非直线传播；第6题选ABC，D错在未强调均匀介质。
+- **练习7（反射定律探究实验）**：用带刻度的硬纸板（中间用透明胶带粘合可前后转动）和小平面镜，配合激光笔验证反射定律；在家可用硬纸壳、透明胶带、小镜子、激光笔自制装置完成。
+- **练习8（反射作图）**：先画法线（虚线，画三段即可），再根据反射角等于入射角画入射或反射光线；可用尺子刻度对称找点法（如法线对准20刻度，反射光上找25刻度点，入射侧对称找15刻度点），作图痕迹保留法线，箭头补全。
+- **练习9（入射角计算）**：反射光线与平面镜夹角40度，则与法线夹角50度，入射角＝反射角＝50度，选A。
+- **练习10（入射角变化）**：入射光线与镜面夹角增大时，入射角减小，反射角随之减小，传播速度不变，选C。
+- **练习11–12（反射角计算）**：入射光线与法线夹角60度时反射角60度；反射光线与入射光线夹角80度时，反射角为40度（角平分线）。
+- **练习13（雨后水潭判断）**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭；可用白纸放小镜子、手电筒垂直照射后斜看验证——镜子变黑、白纸仍亮。
+- **练习14（光路可逆）**：A错，垂直入射时反射角为0度；B对，小明能看到小刚在平面镜中的像，则小刚也一定能看到小明（光路可逆）；C错，漫反射同样遵守反射定律；D错，光在不同介质中速度不同。
+- **练习15–17（镜面反射与漫反射）**：电影院白色银幕对光产生漫反射；教室某些位置看黑板只见光亮看不清粉笔字，是黑板发生镜面反射；电影放映机射到银幕的光经幕布反射进入人眼是漫反射；无论哪种反射都遵守光的反射定律。
+- **练习18（反射现象判断）**：选D，人在河边看到岸边树在水中的倒影是光的反射（平静水面充当平面镜）；A、B属直线传播，C属光的折射。
+- **练习19（平面镜成像实验误差）**：蜡烛到玻璃板距离与像到玻璃板距离不相等，原因是玻璃板与水平面不垂直（或未与预先画好的镜面位置重合）；同一侧看到同一个蜡烛的两个像，原因是玻璃板有厚度，两个面发生反射成像。
+- **练习20（平面镜成像实验）**：用玻璃板代替平面镜的目的是便于确定像的位置；刻度尺用于比较像与物相对镜面的距离；两段完全相同蜡烛用于比较像与物的大小；光屏不能接收到烛焰的像（虚像，实际光线未到达）；物体靠近玻璃板时像的大小不变。
+- **练习21–22（视力表问题）**：视力表距镜子3.5米，像距镜子3.5米，人距镜子1.5米时看到虚像距离为5米；若视力表距镜子3米，人距镜子2米即可。
+- **练习23–24（平面镜成像特点）**：人站在平面镜前1米处，人与像距离2米；人向远离平面镜方向移动，像的大小不变，选C。
 ## 复习重点
-- **光源**：自身能够发光的物体；按来源分为自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
-- **光线**：用带箭头的直线表示，是物理模型，并非真实存在；按形状可分为点光源（如蜡烛）和平行光源（如太阳光）。
-- **光在均匀介质中沿直线传播**：适用条件为同种均匀介质；大气层不均匀时光线发生偏折，表现为太阳越出地平线、星星眨眼等现象。
-- **光速**：真空中为3×10⁸米/秒（约每秒绕地球赤道7圈半）；空气中略慢（约2.99×10⁸米/秒）；水中约为真空的3/4；玻璃中约为真空的2/3。
-- **光的反射定律**：反射光线、入射光线和法线在同一平面内；反射光线和入射光线分居法线两侧；反射角等于入射角；法线垂直于镜面，是入射光线与反射光线夹角的角平分线。
-- **入射角与反射角**：均为光线与法线的夹角；光垂直射到镜面时，入射角和反射角都是0°（易错点：误答90°）。
-- **镜面反射**：平行光射到光滑表面，反射光平行，人眼在特定位置才能看到；黑板反光、平静水面倒影属此类。
-- **漫反射**：平行光射到凹凸不平表面，反射光射向各个方向，人眼在任何位置都能看到；电影银幕、白纸属此类；镜面反射和漫反射都遵守光的反射定律。
-- **光路可逆**：若甲能看到乙在平面镜中的像，则乙也一定能看到甲在平面镜中的像。
-- **平面镜成像特点**：正立、等大、虚像；像与物到镜面距离相等，连线与镜面垂直；虚像无法用光屏接收（实际光线未到达）。
-- **凸面镜**：对光线起发散作用，成正立、缩小的虚像；用于汽车后视镜、丁字路口反光镜。
-- **凹面镜**：对光线起会聚作用，焦点处可汇聚光线；用于手电筒、汽车前大灯、太阳灶、医生额镜；玻璃幕墙形成凹面会聚光线可能造成光污染。
+- **光源**：自身能够发光的物体；按来源分自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
+- **光线**：用带箭头的直线表示，是物理模型，不是真实存在；按形状分点光源（蜡烛）和平行光源（太阳光）。
+- **光在均匀介质中沿直线传播**：适用条件是同一种均匀介质；大气层不均匀时光线发生偏折（日出时太阳看似越出地平线、星星眨眼）。
+- **实例**：三点一线（步枪瞄准、队列排齐、木工看尺子）、激光准直、小孔成像、日食月食、影子形成（皮影戏）。
+- **小孔成像**：成倒立实像（光线实际到达），放大缩小不一定，与孔形状无关；树下光斑是太阳通过树叶缝隙的小孔成像，为缩小的实像（太阳距地球远大于树叶缝隙距地面）。
+- **日食与月食**：日食时太阳、月球、地球在同一直线，月球在中间，1号区域日全食、2/3号区域日偏食、4号区域日环食；月食时地球在中间，月球完全在1号区域为月全食，部分在1号区域、部分在2/3号区域才出现月偏食（月球仅处于2/3号区域只是变暗，不叫月偏食）。
+- **光速**：真空中3×10⁸米/秒（3×10⁵千米/秒，约30万公里/秒），一秒钟绕地球赤道7圈半；空气中约2.99×10⁸米/秒（近似取真空值）；水中约为真空的3/4，玻璃中约为真空的2/3；光本质是电磁波。
+- **光的反射定律**：反射光线、入射光线和法线在同一平面内（共面）；反射光线和入射光线分居法线两侧；反射角等于入射角；垂直射到镜面时入射角和反射角均为0度。
+- **法线**：过入射点垂直于镜面的辅助线，是入射光线与反射光线夹角的角平分线，画虚线，不是真实存在；引入法线是为后续折射学习作准备。
+- **镜面反射**：平行光射到光滑表面，反射光平行；易造成反光（如黑板反光、商场玻璃隔断撞人）；一束光射到平面镜上，只有反射光恰好进入人眼才能看见。
+- **漫反射**：平行光射到凹凸不平表面，反射光射向各个方向；生活中大多数反射是漫反射（黑板、电影银幕、投影幕布、人眼看见物体）；镜面反射和漫反射都遵守光的反射定律。
+- **平面镜成像特点**：正立、等大、虚像；像与物连线垂直镜面，像距等于物距；虚像不能用光屏接收（实际光线未到达镜后）。
+- **平面镜成像原理**：根据光的反射定律，反射光线反向延长线的交点即像点；平静水面、光滑金属表面可充当平面镜。
+- **凸面镜**：对光线起发散作用，成正立、缩小的虚像；用于汽车后视镜、丁字路口反光镜；视觉上物体显得比实际远。
+- **凹面镜**：对光线起会聚作用，平行光会聚于焦点；用于手电筒（电珠在焦点）、汽车前大灯、探照灯、太阳灶、医生额镜（中间镂空便于观察）；阿基米德用平面镜围成凹面烧敌船。
+- **玻璃幕墙光污染**：凹面玻璃幕墙会聚光线，可能烧死树木、引燃电线，且反射声音造成噪音；设计费按建筑成本计算是设计师倾向用玻璃幕墙的原因之一。
 ## 学习建议
-- **自制小孔成像实验**：用纸杯底部用针扎小孔（勿用钉子扎大孔），杯口蒙塑料布，点燃蜡烛置于小孔前方，可在塑料布上看到倒立的火苗像；体会像与孔形状无关。
-- **自制反射定律探究装置**：用硬纸壳（中间用透明胶带粘合可前后转动）、小平面镜和激光笔，在纸壳上画好刻度，即可在家验证光的反射定律。
-- **自制平面镜成像实验**：白纸上立一块透明玻璃，前方点燃蜡烛，后方移动未点燃蜡烛至像的位置，记录两蜡烛位置，可验证像与物到镜面距离相等、连线与镜面垂直。
-- **雨后水潭判断实验**：白纸上放一面小镜子，用手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的，直观理解镜面反射与漫反射的区别。
-- **购买激光笔**：两元店或十元店即可买到，激光笔光线强度大、线直，便于观察直线传播和反射实验，不必买昂贵型号。
-- **保护视力提醒**：主讲人强调长时间用眼、教室拉窗帘、写字姿势不良等都会导致近视；建议多到户外活动，避免长时间盯屏幕，注意用眼卫生。</t>
+- **自制小孔成像实验**：用纸杯（或易拉罐）底部用针扎一个小孔（不要用钉子扎大孔），前面用塑料布蒙上，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像；体会像与孔形状无关。
+- **自制反射定律实验**：用硬纸壳（中间用透明胶带粘合可前后转动）、小平面镜、画好均匀格子的纸和激光笔，在家即可验证光的反射定律；激光笔在二元店即可买到，不必买贵的。
+- **自制平面镜成像实验**：白纸上立一块透明玻璃板，用两支蜡烛（或两枚跳棋子），一支点燃放在玻璃板前，移动另一支到像的位置，记录位置后可验证像与物连线垂直镜面、像距等于物距。
+- **验证镜面反射与漫反射**：白纸上放一面小镜子，用手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的——镜子发生镜面反射光返回，白纸表面粗糙发生漫反射。
+- **观察生活中的光学现象**：夏天观察大杨树底下的光斑（太阳的小孔成像，风刮时光斑晃动，多为椭圆形）；雨后夜晚判断水潭位置（迎着月光走亮处是水潭，背着月光走暗处是水潭）；观察停车场丁字路口反光镜（凸面镜，成正立缩小虚像）。
+- **保护眼睛**：主讲人提醒长时间看屏幕、判卷子、写字姿势不良都会导致视力下降；教室整天拉窗帘、缺乏户外光照是近视率高的原因之一；建议多到户外看远处，避免长时间近距离用眼。</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>82.2</v>
+        <v>81</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25691/8398</t>
+          <t>25691/7433</t>
         </is>
       </c>
     </row>
@@ -4633,135 +4636,105 @@
       <c r="C13" t="inlineStr">
         <is>
           <t># 课程概况
-电气工程基础是电气工程及其自动化专业的入门课程，本次为课程导论及第一章绪论部分。课程提出两个教学目标：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及其与电力系统整体的关系，建立电力系统的整体概念；二是掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术与计算方法。课程要求前修电路理论和电机学知识，特别是变压器和同步电机相关内容；后续重要课程包括电力系统分析、电力系统机电保护、电力系统自动化和高电压技术。本次课程主要内容包括：梳理交直流输电发展简史及交直流之争，论证三相交流输电的优势；从单机供电可靠性差出发，推导电力系统形成过程，给出电力系统、电力网、动力系统的定义；按规模将电网分为地方、区域、超高压远距离输送三类，并介绍变电站按电压等级和功率流向的分类方法。第一章为全课程概念最多、最重要的章节，重点掌握基本概念、电力系统特点与要求、电能质量指标及常用接地方式，难点在于有功无功动态平衡、额定电压规定和中心点接地方式。
+本课程为电气工程基础，是学生进入专业课后的第一门入门课。课程教学目的有二：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与整体关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行、管理方面的基础理论、基本技术与计算方法。前修课程要求电路理论和电机学知识，特别是变压器和同步电机；后续重要课程包括电力系统分析、继电保护、自动化、高电压技术。第一章为重点章节，涵盖基本概念、特点与要求、电能质量指标、常用接地方式，并指出三个学习难点：电能不能大量储存决定的有功无功动态平衡、额定电压规定繁杂、各种中性点接地方式对后续章节的影响。课程还梳理了交直流输电发展史，从1874年俄国4.5公里直流线路到2009年中国1000千伏特高压交流投运，并讲解三相交流输电优势、电力系统形成过程，以及电力系统、电力网、动力系统定义和电网分类。
 # 核心知识点梳理
-## 课程目标与定位
+## 课程目标与学习要求
 - **课程定位**：电气工程基础是进入专业课后的**第一门课**，属于专业入门课，对今后工作非常重要。
 - **教学目标一**：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与电力系统整体之间的关系，建立电力系统的整体概念。
-- **教学目标二**：掌握电力系统在**分析、设计、运行、管理**方面的基础理论、基本技术及基本计算方法。
+- **教学目标二**：掌握电力系统在分析、设计、运行、管理方面的**基础理论、基本技术及基本计算方法**。
 - **前修课程要求**：需了解电路理论和电机学知识，特别是**变压器和同步电机**相关知识要求较高；有欠缺的同学应课后补充相关内容。
-- **重要后续课程**：电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。
-## 第1章学习内容与难点
-- **学习内容一**：掌握电力系统若干基本概念，包括电力系统、电力网、动力系统和变电站等相关概念。
-- **学习内容二**：理解电力系统的特点，以及由特点引起的电力系统设计、运行等方面的基础理论。
-- **学习内容三**：理解对电力系统提出的要求，涉及电力系统运行、设计和维护各方面。
-- **学习内容四**：掌握电力系统电能质量指标，包括**国家标准**对这些指标的各种规定范围。
-- **学习内容五**：了解电力系统常用接地方式，特别是**工作接地（中性点接地方式）**的不同特点。
-- **难点一** ⭐：由电力系统特点引出的基本原理，如**电能不能大量储存**决定了电力系统**有功功率和无功功率的动态平衡**问题，是运行调整和设计的基础。
-- **难点二** ⭐：电力系统**额定电压的规定**繁杂，需注意把规定搞清楚。
-- **难点三** ⭐：各种**中性点接地方式**直接影响后续多个章节内容，学习起来较困难。
-- **学习方法一**：对基本概念注意其**内涵和外延**，并适当记忆。
-- **学习方法二**：从电力系统特点和要求出发，**从最基础原理推导**，不要死记结论（结论在使用条件变化时会失效）。
-- **学习方法三**：注意寻找额定电压规定之间的**基本规律**。
-- **学习方法四**：注意**比较不同中性点接地方式**之间的特点。
-## 直流输电发展简史
-- **早期直流试验**：电力发展从直流开始而非交流；福泰勒用2000米导线连接瓦斯发电机，拖动直流发电机、电动机和带水泵的电动机，证明直流远距离（两公里）输电可行。
-- **1874年**：俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率**4.5千瓦**，后用于有轨电车的原始工业试验。
-- **1882年**：法国德普勒架设首条**57公里**直流试验线路，采用电报线传输，首端电压343伏、末端850伏，输送功率**200瓦**，损耗**78%**，将水电站直流发电机电力送至博览会。
-- **1883年**：德普勒从法国南部进行**14公里**输电试验，输送功率**1.1千瓦**，从瓦利尔书店到巴黎56公里，损耗**55%**。
-- **1882年10月**：英国科学家发明直流**三线制系统**，外线与中线间电压110伏，两外线间220伏；后扩展到5根线形成直流无限制系统。
-- **直流输电限制**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难，限制远距离大容量输电。
-- **19世纪末**：法国科学家方剑在送端将多台直流发电机**串联**以提高电压，将**75千瓦**电力输送**75千米**。
-- **20世纪初期**：瑞典科学家在串联直流发电机上装**短路器**，使任意发电机投切不停电；此后20多年间建成**15条**直流输电线路。
-- **1906年**：投运法国慕尼黑水电厂到里昂的**180公里、57千伏、4700千瓦**直流线路。
-- **1927年**：改建为**260公里、125千伏、19000千瓦**，接入两座水电站。
+- **后续重要课程**：电力系统分析、电力系统继电保护、电力系统自动化、高电压技术四门课。
+- **第一章学习内容**：①电力系统若干基本概念（电力系统、电力网、动力系统、变电站）；②电力系统的特点及由此引起的基础理论；③对电力系统提出的要求；④电能质量指标及国家标准规定范围；⑤常用接地方式，特别是工作接地（中性点接地方式）的不同特点。
+- **学习难点一** ⭐：由电力系统特点引出的基本原理，如**电能不能大量储存**决定了电力系统**有功功率和无功功率的动态平衡**问题，是运行调整和设计的基础。
+- **学习难点二** ⭐：电力系统**额定电压的规定**繁杂，需注意把规定搞清楚。
+- **学习难点三** ⭐：各种**中性点接地方式**直接影响后续多个章节内容，学习难度较大。
+- **学习方法**：①基本概念注意内涵和外延并适当记忆；②从电力系统特点和要求出发、从最基础原理推导，**不要死记结论**（使用条件变化时结论将失效）；③寻找额定电压规定之间的基本规律；④比较不同中性点接地方式之间的特点。
+## 电力发展简史
+- **直流输电起源**：电力发展从直流开始而非交流；福泰勒用2000米导线连接瓦斯发电机，拖动直流发电机、电动机和带水泵的电动机，证明直流远距离（约2公里）输电可行。
+- **1874年俄国试验**：俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率**4.5千瓦**，后用于有轨电车的最原始工业试验。
+- **1882年德普勒试验**：法国德普勒架设首条**57公里**直流试验线路，采用电报线传输，首端电压343伏、末端850伏，输送功率200瓦，损耗**78%**，将水电站直流发电机电力送至博览会。
+- **1883年德普勒试验**：从法国南部进行**14公里**输电试验，输送功率1.1千瓦，从瓦利尔书店到巴黎56公里，损耗55%。
+- **直流三线制发明**：1882年10月英国科学家发明直流输电三线制系统，外线与中线间电压110伏、两外线间220伏，后扩展到5根线形成直流无限制系统。
+- **直流输电早期局限**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难，限制远距离大容量输电。
+- **串联直流发电机方案**：19世纪末法国科学家方剑在送端串联多台直流发电机以提高电压，将75千瓦电力输送75千米；20世纪初瑞典科学家加装短路器使任意发电机投切不停电，此后20多年建成**15条**直流输电线路。
+- **1906年直流线路**：法国慕尼黑水电厂到里昂的**180公里、57千伏、4700千瓦**线路投运；1927年改建为**260公里、125千伏、19000千瓦**，接入两座水电站。
 - **直流输电制约因素**：设备复杂、运行方式复杂、造价高、可靠性差。
-- **1954年**：瑞典本土与哥特兰岛间建成**世界第一个工业用海底电缆**直流工程，电压**100千伏**、**96公里**，采用汞弧阀换流。
-- **1970年**：瑞典本土与哥特兰岛间扩建**50千伏、1万千瓦**晶闸管换流阀试验工程。
-- **1972年**：世界上第一个**晶闸管换流阀背靠背直流工程**在加拿大投运。
-- **中国直流工程**：第一个直流输电工程连接**舟山群岛与浙江定海**电网；第二个是1989年**葛上直流**（葛洲坝电厂到上海），±500千伏。
-- **云广直流**：今年6月投运的**±800千伏特高压直流工程**，为标志性工程。
-## 交流输电发展简史
-- **变压器前身**：英国法拉第的电磁感应原理；美国亨利用多匝线圈作原边、少匝线圈作副边，使高电压感应出低电压。
-- **1876年**：俄国科学家发明**单相变压器**，主要用于照明。
-- **变压器串联问题**：法国和英国科学家联合将多台变压器串联到输电线路中，当电弧灯负荷变化时输电电压受干扰。
-- **1883年**：美国特斯拉制造出**感应电机**，为标志性成果。
-- **1885年**：匈牙利科学家设计多台变压器**并联运行**连接方式，使并联运行成为可能。
-- **交直流之争**：爱迪生与凯尔文主张直流电，理由为直流电效率高、交流电有危险性；爱迪生购买威斯汀豪斯公司的交流发电机卖给监狱给死刑犯执行死刑以证明交流电危险。
-- **交流电主张**：威斯汀豪斯和特斯拉主张交流电，因交流电易用变压器升压降压，可在高电压下减少电能损失；交流发电机制造业发展为交流输电做了准备。
-- **1886年**：威斯汀豪斯在美国麻省进行**1.2千米、30千伏**交流输电示范；同年又在意大利建成**17英里、2千伏**高压输电线路。
-- **1886年**：俄国科学家发明**三相交流电、三相交流输电和三相异步电动机**。
-- **交直流之争标志**：从法国到德国的交流输电线路（常被认为是第一条交流输电线路），水电站安装三相发电机和升压变压器，升压后送到德国，在法兰克福建两座降压变电站——一座供展览会照明，另一座供**100马力三相异步电动机**（用于人工瀑布离心泵）。
-- **绝缘技术进展**：1898年发明针式绝缘子，美国加利福尼亚输电电压升至**33千伏**；1906年发明悬式绝缘子，建成**110千伏**高压输电。
-- **1912年**：发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成**154千伏**线路。
-- **1923年**：均压环技术应用，建成**220千伏**输电线路。
-- **1936年**：美国**287千伏**线路投运。
-- **1952年**：瑞典建成**380千伏**线路，**第一次采用分裂导线**。
-- **1956年**：苏联**400千伏**双回线路（平行双回线）投入运行。
-- **1965年**：加拿大建成**735千伏**输电系统。
-- **1969年**：美国**765千伏**线路并入电网。
-- **1985年**：苏联**1150千伏**特高压线路投运，后降压至500千伏运行。
-- **中国电压等级发展**：220千伏于**1941年**投运，330千伏于**1972年**投运，500千伏于**1981年**投运，**1000千伏交流特高压于2009年投运**（国家标志性首次投运成果）。
-- **直流重新受关注**：交流大电网稳定问题突出后，直流在联网中的优势显现，用于电网与电网之间的连接。
+- **变压器前身**：英国法拉第电磁感应原理；美国亨利用多匝线圈做原边、少匝线圈做副边，使高电压感应出低电压。
+- **单相变压器与并联运行**：1876年俄国科学家发明单相变压器（主要用于照明）；法国和英国科学家联合将多台变压器串联到输电线路中，发现负荷变化时输电电压受干扰；1885年匈牙利科学家设计多台变压器**并联运行**连接方式。
+- **感应电机**：1883年美国特斯拉制造出感应电机，具有标志性意义。
+- **交直流之争**：爱迪生和凯尔文主张直流电，理由为直流效率高、交流有危险性（爱迪生购买威斯汀豪斯公司的交流发电机卖给监狱给死刑犯执行死刑以证明危险性）；威斯汀豪斯和特斯拉主张交流电，理由为交流电易用变压器升压降压、可减少电能损失。
+- **交流输电早期示范**：1886年威斯汀豪斯在美国麻省进行**1.2千米、30千伏**交流输电示范；同年又在意大利建成17英里、2千伏高压输电线路；1886年俄国科学家发明三相交流电、三相交流输电和三相异步电动机。
+- **交直流之争标志性工程**：从法国到德国的交流输电线路（被认为是第一条交流输电线路），水电厂安装三相发电机和升压变压器，升压后送到德国，在法兰克福建两座降压变电站，一座供展览会照明、另一座供100马力三相异步电动机（用于人工瀑布离心泵）。
+- **交流电压等级提升时间线**：1898年发明针式绝缘子，美国加利福尼亚电压等级提高到**33千伏**；1906年发明悬式绝缘子，建成**110千伏**高压输电；1912年发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成**154千伏**线路；1923年均压阀技术应用，建成**220千伏**线路；1936年美国**287千伏**线路投运；1952年瑞典建成**380千伏**线路（**首次采用分裂导线**）；1956年苏联**400千伏**双回线路投运；1965年加拿大建成**735千伏**输电系统；1969年美国**765千伏**线路并入电网；1985年苏联**1150千伏**特高压线路投运（后降压至500千伏运行）。
+- **中国交流输电时间线**：1941年**220千伏**投运；1972年**330千伏**投运；1981年**500千伏**投运；2009年**1000千伏**特高压交流投运（国家标志性首次投运成果）。
+- **直流输电复兴**：交流大电网稳定问题突出后，直流在联网中的优势显现，重新用于电网与电网之间的连接。
+- **1954年海底电缆直流工程**：瑞典本土与哥特兰岛之间建成**世界首个工业海底电缆直流工程**，电压等级**100千伏、96公里**，采用汞弧阀技术。
+- **晶闸管换流阀发展**：1970年瑞典本土与哥特兰岛扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年**世界首个晶闸管换流阀背靠背直流工程**在加拿大投运。
+- **中国直流输电工程**：首个直流工程连接**舟山群岛与浙江定海**电网；1989年**葛上直流**（葛洲坝电厂到上海）±500千伏；今年6月投运**云广直流**±800千伏特高压直流工程。
+- **推荐阅读**：推荐三本书供学生课后阅读，了解电力发展基本史。
 ## 三相交流输电优势
-- **三相系统优点一**：易于产生旋转磁场，三相电动机容易做驱动。
-- **三相系统优点二**：瞬时功率恒定，不随时间变化。
-- **三相系统优点三**：输电线路导线量（金属消耗量）最少。
+- **三相系统优点一**：易于产生**旋转磁场**，三相电动机容易做驱动。
+- **三相系统优点二**：**瞬时功率恒定**，不随时间变化。
+- **三相系统优点三**：输电线路所用**导线量（金属消耗量）最少**。
 - **应用范围**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内电力系统大多数高压、超高压、特高压输电采用三相交流，**联网时才采用直流**。
-- **三相三线制效率**：在直流传输方式和其他交流传输方式中，**三相三线制传输效率最高**。
-- **金属消耗量比较**：三相三线制全截面为一根导线截面乘以3，在同等功率和功率因数下**金属消耗量最小**。
-- **结论**：因效率最高和金属消耗量最小两个原因，三相三线制在交流输电领域得到广泛应用，至今仍采用。
-## 电力系统的形成
-- **单机供电缺点**：一台发电机向附近负荷供电，发电机出问题负荷即停电，**供电可靠性差**（如街边小柴油发电机向商铺供电）。
-- **提高可靠性方法**：将两台发电机并联，一台出问题时另一台可带重要负荷，连接越来越多形成网络。
-- **输电线路参数问题**：导线有**电阻和电抗**两个重要参数，传输功率时产生**电压损耗和功率损耗**；阻抗越大、电流越大，损耗越大，因此输电线路不能太长。
-- **提高电压原理**：传输有功功率一定时，电压升高则电流减小，线路有功损耗（I²R）和电压降落（IZ）均减小，输电距离可变长。
-- **交流升压手段**：采用**变压器**，送端升压、受端降压，中间电压升高后距离损耗降低。
-- **电力系统雏形**：近距离（几十到几百米）发电机可直接相连，远距离则升压传输，多台发电机共同供电形成电力系统雏形。
-- **系统化好处一**：一台发电机停运影响不大，只需发电机数目多于负荷即可保证供电。
-- **系统化好处二**：可装大机组向大片区域供电，完成从**小发电机组向大发电机组**的转变，直接带来经济效益。
-- **远距离输电问题**：距离很长时（如湖北送电华东、云贵送电两广），中间负荷可在输电线路中间装设**变电站**降压供电；稳定问题也可在变电站装设备调整。
-## 电力系统、电力网与动力系统定义
-- **电力系统定义**：由**发电机、变压器、输电线路和用电设备**构成的整体，完成电能**生产、输送、分配、消耗**四个方面的职能，由发电、输电、配电、用电四个环节组成。
-- **电力网定义**：由**变压器和输电线路**构成的网络，即电力系统中去除发电机和用电设备后的部分。
-- **动力系统定义**：在电力系统基础上加上发电厂动力部分，如火电厂的**锅炉、汽机及煤炭输送处理系统**，水电厂的**水轮机、水坝、水库**等。
-- **概念辨析**：行业中最常说的是**电力网**和**电力系统**两个概念，动力系统概念现在很少说；*电力系统比电力网多了发电机和用电设备，动力系统比电力系统多了动力部分*。
-## 电网分类
+- **效率论证**：三相三线制传输效率最高；与单相三线制和对称n相n线制比较，同等功率和功率因数下**金属消耗量最小**（全截面为一根导线截面×3）。
+- **结论**：因效率最高和金属消耗量最小，三相三线制在交流输电领域得到广泛应用，目前仍采用此输电方式。
+## 电力系统的形成与定义
+- **单机供电缺陷**：一台发电机向附近负荷供电，发电机出问题负荷即停电，**供电可靠性差**（如街边小柴油发电机向商铺供电）。
+- **并联提高可靠性**：将多台发电机并联连接，一台出问题时另一台可带重要负荷，可靠性提高。
+- **线路损耗限制距离**：输电线路有**电阻和电抗**两个重要参数，传输功率时产生**电压损耗和功率损耗**；阻抗越大、电流越大，损耗越大，输电线路不能太长。
+- **升压解决远距离输电**：传输有功功率一定时，电压升高则电流减小，线路有功损耗（I²R）和电压降落（IZ）均减小，输电距离可变长；交流系统通过**变压器**升压（一侧升、另一侧降）。
+- **电力系统雏形**：近距离（几十到几百米）发电机直接相连，远距离升压传输，多台发电机共同供电，形成电力系统雏形。
+- **电力系统形成的好处**：①一台发电机停运影响不大，只需发电机数目多于负荷；②可装大机组向大片区域供电，供电范围扩大，**直接带来经济效益**。
+- **输电线路中间变电站**：远距离输电（如湖北送电华东、云贵送电两广）时，线路中间装设变电站降压向当地用户供电，并可引接部分负荷；稳定问题也可通过变电站设备调整。
+- **电力系统定义**：由**发电机、变压器、输电线路和用电设备**构成的整体，完成电能**生产、输送、分配、消耗**四个环节的职能，由发电、输电、配电、用电四个环节组成。
+- **电力网定义**：电力系统中**去除发电机和用电设备**的部分，即变压器和输电线路构成的网络。
+- **动力系统定义**：电力系统加上发电厂动力部分（火电厂的锅炉、汽机、煤炭输送处理系统；水电厂的水轮机、水坝、水库等）。
+- **概念辨析**：行业中最常用的是**电力网**和**电力系统**两个概念，动力系统概念较少使用；电力系统比电力网多了发电厂和用电设备。
+## 电网分类与变电站分类
 - **地方电力网**：向固定地方供给电能的网络，电压等级一般在**110千伏及以下**（早期定义35千伏及以下），供电半径**20~50公里**。
 - **区域电力网**：电压等级**110、220千伏**及少量500千伏，供电半径**超过50公里**，联系较多发电厂和负荷中心的网络。
-- **超高压远距离输送网络**：电压等级**500千伏或1000千伏**（东北有330千伏），任务是把发电厂电能送到负荷中心，距离很远，构成**跨省跨地区大型电力系统**。
-- **实例一**：武汉电网属**地方电力网**，主要供电电压110千伏和35千伏，少数地方出现220千伏，供电半径一般在50公里以内。
-- **实例二**：华中电网属典型**区域电网**，华中几省紧密联系，供电半径较大。
-- **实例三**：葛上直流、三峡到上海输电线路属**超高压远距离输电网络**，连接华中与华东。
-- **实例四**：山西晋东南到湖北荆门的特高压系统，跨三个省，连接华北电网和华中电网，属超高压远距离输送网络。
-- **电压等级变化规律**：随着电网发展和电压等级提高，各级电网所用电压等级会发生变化，**一般趋向提高**；变电站地位也随之变化。
-## 变电站分类
-- **按最高电压等级分类**：以站内最高电压等级命名，如华工变电站为**10千伏变电站**（10千伏变380伏），关山变电站为**220千伏变电站**，凤凰山变电站为**500千伏变电站**。
-- **按主要功率流向分类**：以**最主要的功率**流向为准——大部分功率从高压侧流向低压侧为**降压变电站**；发电厂内大部分功率从低压侧升到高压侧为**升压变电站**。
+- **超高压远距离输送网络**：电压等级**500千伏或1000千伏**（东北有330千伏网络），任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统。
+- **电网分类实例**：武汉电网属**地方电力网**（主要供电电压110千伏和35千伏，少数220千伏，供电半径50公里以内）；华中电网是典型**区域网**（华中几省紧密联系）；葛上直流、三峡到上海输电线路属**超高压远距离输送网络**；山西晋东南到湖北荆门特高压系统跨三个省、连接华北和华中电网，属超高压远距离输送网络。
+- **电压等级动态变化**：随着电网发展，各级电网所用电压等级会提高，变电站地位也随之变化。
+- **变电站按最高电压等级分类**：华工变电站最高电压**10千伏**（10千伏变380伏）；关山变电站**220千伏**；凤凰山变电站**500千伏**。
+- **变电站按主要功率流向分类**：**降压变电站**——大部分功率从高压侧流向低压侧；**升压变电站**——发电厂内大部分功率从发电机低压侧升压到高压侧。
 # 课堂互动与答疑
 **学生**：为什么我国电力系统主要采用交流三相三线制，而不是直流输电？
-**教师**：三相三线制在传输效率上最高，同等功率和功率因数下金属消耗量最小；三相交流还易于产生旋转磁场、瞬时功率恒定。国内高压、超高压、特高压输电基本采用三相交流，仅在电网联网时才采用直流方式。
-**学生**：电力系统、电力网和动力系统三个概念有什么区别？
-**教师**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配、消耗四个环节；电力网仅含变压器和输电线路，不含发电机和用电设备；动力系统在电力系统基础上再加发电厂动力部分（锅炉、汽机、水轮机等）。行业中最常用的是电力网和电力系统两个概念。
-**学生**：地方电网、区域电网和超高压远距离输送网络如何区分？
-**教师**：按电压等级和供电半径区分：地方电网电压110千伏及以下（早期35千伏及以下），供电半径20~50公里；区域电网电压110、220千伏及少量500千伏，供电半径超50公里；超高压远距离输送网络电压500千伏或1000千伏（东北有330千伏），构成跨省跨地区大型电力系统。武汉电网属地方电网，华中电网属区域电网，三峡到上海线路属超高压远距离输送网络。
-**学生**：为什么输电距离不能太长，提高电压后就能送得更远？
-**教师**：输电线路有电阻和电抗，传输功率时产生电压损耗和功率损耗，距离越长损耗越大、电压降得越低。提高电压后，传输相同功率时电流减小，线路上的有功损耗（I²R）和电压降落（IZ）随之降低，输电距离就能变长。交流升压采用变压器，送端升压、受端降压。
+**教师**：三相交流系统有三个优点：易于产生旋转磁场，便于三相电动机驱动；瞬时功率恒定，不随时间变化；同等功率和功率因数下输电线路金属消耗量最少。三相三线制传输效率最高，金属消耗量最小，因此除室内配电等小功率场合采用单相交流外，其余基本采用三相交流。直流仅在电网联网时采用，如葛上直流±500千伏、云广直流±800千伏特高压直流工程。
+**学生**：电力系统、电力网和动力系统这三个概念有什么区别？
+**教师**：电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配、消耗四个环节；电力网是电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络；动力系统是在电力系统基础上再加入发电厂动力部分，如火电的锅炉汽机、水电的水轮机水坝等。行业中最常用的是电力网和电力系统两个概念，动力系统较少使用。
+**学生**：地方电力网、区域电力网和超高压远距离输送网络如何区分？
+**教师**：地方电力网向固定地方供电，电压等级一般在110千伏及以下（早期35千伏及以下），供电半径20~50公里，如武汉电网；区域电力网电压等级为110、220千伏及少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心，如华中电网；超高压远距离输送网络电压等级为500千伏或1000千伏（东北有330千伏），任务是将电能送到负荷中心，构成跨省跨地区大型电力系统，如三峡到上海的输电线路。
 # 课后任务与学习建议
+## 课堂练习
+未提及
 ## 复习重点
-- **电力系统四个环节**：掌握发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念。
-- **电力系统、电力网、动力系统定义**：电力系统＝发电机＋变压器＋输电线路＋用电设备，完成电能生产、输送、分配、消耗；电力网＝变压器＋输电线路（不含发电机和用电设备）；动力系统＝电力系统＋发电厂动力部分（锅炉、汽机、水轮机等）。
-- **电力系统特点及要求**：电能不能大量储存，决定有功功率和无功功率的动态平衡问题，是运行调整和设计的基础；理解由特点引起的设计、运行、维护方面的基础理论。
-- **电能质量指标**：掌握国家标准对电能质量指标规定的各种范围。
-- **额定电压规定**：规定繁杂，注意寻找额定电压规定之间的基本规律，注意随电网发展各级电网电压等级会提高。
-- **中心点接地方式**：了解电力系统常用接地方式，特别是工作接地（中心点接地方式）的不同特点；该内容直接影响后续多个章节，学习较困难。
-- **电网分类**：地方电力网（110千伏及以下，早期35千伏及以下，供电半径20~50公里）、区域电力网（110、220千伏及少量500千伏，供电半径超50公里）、超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，跨省跨地区）。
-- **变电站分类**：按最高电压等级分类（如10千伏、220千伏、500千伏变电站）；按主要功率流向分为降压变电站（高压侧流向低压侧）和升压变电站（低压侧流向高压侧）。
+- **电力系统四个环节**：发电、输电、配电、用电的构成与工作原理，以及与电力系统整体的关系，需建立电力系统整体概念。
+- **电力系统定义**：发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个环节的职能。
+- **电力网定义**：电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络；电力系统比电力网多了发电厂和用电设备。
+- **动力系统定义**：电力系统加上发电厂动力部分（如火电厂的锅炉汽机及煤炭输送处理系统、水电厂的水轮机水坝水库），行业中最常用的是电力网和电力系统概念。
+- **电力系统特点**：电能不能大量储存，决定了电力系统有功功率和无功功率的动态平衡问题，是进行运行调整和设计的基础原理。
+- **电能质量指标**：包括国家标准对各种电能质量指标规定的范围，需掌握其规定内容。
+- **常用接地方式**：重点是工作接地即中性点接地方式的不同特点，直接影响后续多个章节内容。
+- **额定电压规定**：规定繁杂，需注意寻找额定电压规定之间的基本规律，并注意随电网发展各级电网电压等级会提高。
+- **电网分类**：地方电力网（110千伏及以下，供电半径20~50公里）、区域电力网（110、220千伏及少量500千伏，供电半径超50公里）、超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，构成跨省跨地区大型电力系统）。
+- **变电站分类**：按最高电压等级分类（如华工变电站10千伏、关山变电站220千伏、凤凰山变电站500千伏）；按主要功率流向分为升压变电站和降压变电站。
 - **三相交流输电优势**：易于产生旋转磁场、瞬时功率恒定、输电线路金属消耗量最少；三相三线制传输效率最高，金属消耗量在同等功率和功率因数下最小。
 ## 学习建议
-- **补充前修知识**：对电路理论和电机学有欠缺的同学，应下去补充相关内容，特别是变压器和同步电机的相关知识，本课程要求较高。
-- **掌握基本概念方法**：注意概念的内涵和外延，并适当结合实际；从电力系统的特点和要求出发，从最基础原理推导，不要死记结论——使用条件变化时结论可能失效。
-- **梳理额定电压规律**：注意寻找额定电压规定之间的基本规律，避免因规定繁杂而混淆。
-- **比较接地方式特点**：注意比较各种不同中心点接地方式之间的特点，为后续章节学习打基础。
-- **课后阅读电力发展史**：作为电气专业学生应了解电力发展的基本历史，推荐三本书供课后阅读，了解交直流输电发展历程及国内外电压等级提升过程。</t>
+- **补充前修知识**：对电路理论和电机学知识有欠缺的同学，应补充相关内容，特别是变压器和同步电机的相关知识，本课程对此要求较高。
+- **掌握基本概念方法**：注意概念的内涵和外延，并适当结合实际；从电力系统的特点和要求出发，从最基础的原理进行推导，不要只记结论——使用条件变化时结论可能失效。
+- **梳理额定电压规律**：注意寻找额定电压规定之间的基本规律，不要死记硬背繁杂的规定。
+- **比较接地方式特点**：注意比较各种不同中性点接地方式之间的特点，学完章节后仔细体会。
+- **阅读电力发展史**：作为电气专业学生应了解电力发展的基本发展史，主讲人推荐三本书供课后阅读，了解交直流输电发展历程及关键工程节点。</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>87.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11163/7315</t>
+          <t>11163/6708</t>
         </is>
       </c>
     </row>
@@ -4842,45 +4815,63 @@
       <c r="C14" t="inlineStr">
         <is>
           <t># 知识主题与概述
-皮卡在视频中评论了Stack Exchange上关于调和级数发散性的证明，首先介绍了级数收敛与发散的定义，然后逐一评述了网友的证明方法。第一个证明通过分组估计，每组和大于1/2，从而证明发散；皮卡补充了柯西凝聚判别法，指出其证明思路与分组估计完全一致，可推广到非负不增序列。第二个证明使用不等式e^{1/k}&gt;1+1/k，通过连乘积得到H_n&gt;log(n+1)，皮卡认为该证明技巧性强但故弄玄虚，本质与积分估计法相同。积分估计法用积分近似H_n，证明H_n&gt;log(n+1)；差分法使用Stolz定理，通过差分极限为1证明H_n/log n→1，但皮卡认为差分法不自然，因为需要预先知道结果。皮卡总结认为调和级数发散，但不同证明方法有优劣，某些证明故弄玄虚，妨碍理解。
+本期视频围绕调和级数∑1/n的收敛与发散问题展开，核心议题是评论Stack Exchange上网友对该经典数学问题的多种证明方法。整体逻辑框架按「定义 → 方法评论 → 结论倾向」推进：先介绍级数收敛与发散的定义，随后逐一评点网友的分组证明、柯西凝聚判别法、积分估计法、差分法及Stolz定理证明，最后给出整体立场。皮卡认为调和级数发散的本质是简单的，部分证明方法技巧性强、有故弄玄虚之嫌，反而妨碍理解；他同时指出某些证明需预先知道结果，属于「先射箭后画靶」的不自然思路。
 # 核心概念
-## 级数收敛与发散
-- **收敛**：对于正向级数，若存在固定实数a，使得所有部分和s_n都小于a，则级数收敛。
-- **发散**：若部分和s_n大于某个无界递增的b_n，即对任意大的数b，总能通过增大n使b_n超过b，则级数发散。
-## 分组估计法
-- 第一个网友的证明：将调和级数分组，每组和大于1/2，如1/2+1/3&gt;1/2，1/4+1/5+1/6+1/7&gt;1/2，以此类推，从而证明发散。
-- 皮卡指出，这种分组求和思路与高斯求和（1+2+…+100）类似，核心是发现具有良好性质的组，将求和问题转化为计数问题。
+## 调和级数的收敛与发散
+- **级数收敛的定义**：对于正向级数，若所有部分和`sn`都小于某个固定实数`a`（上界），即无论`n`取多大，`sn`始终被该上界控制，则称级数收敛。
+- **级数发散的定义**：若部分和`sn`大于某个单向递增且永无止境的下界`bn`，即任意给定一个数`b`，总能通过增大`n`使`bn`超过`b`，则称级数发散。
+- **调和级数**：形如`1 + 1/2 + 1/3 + … + 1/n`的级数，其部分和记作`hn`（英文为`harmonic`），是调和序列的部分和。
+## 分组求和证明
+- **核心思路**：将调和级数的项按`1`、`1/2+1/3`、`1/4+1/5+1/6+1/7`、`1/8~1/15`等分组，每组和都大于`1/2`。
+- **关键推演**：第一组为`1`；第二组`1/2+1/3`大于两个`1/4`之和即`1/2`；第三组四项均大于`1/8`，`4×1/8=1/2`；第四组八项均大于`1/16`，`8×1/16=1/2`。由于级数包含任意多组，每组和均大于`1/2`，故部分和无上界，级数发散。
+- **皮卡评点**：这是微积分前几堂课常讲的方法，也是网上很多人会展示的证明。
 ## 柯西凝聚判别法
-- 证明过程与分组估计完全一致，通过分组取上界或下界，将原级数的收敛性转化为加速序列的收敛性。
-- 适用于非负不增序列，如调和级数∑1/n的收敛性等价于∑2^k·(1/2^k)=∑1，后者显然发散。
+- **定义**：对于非负不增序列的级数，其收敛发散性质等价于`∑2^k·a(2^k)`的收敛发散性质。
+- **证明思路**：与分组求和证明完全一致——通过分组，对每组取上界或下界进行估计，从而得到对整个部分和的估计。
+- **应用价值**：适用于增长很慢、不易直接判断收敛性的级数。例如调和级数经凝聚后等价于`∑2^k·(1/2^k)=∑1`，即无穷个`1`相加，显然发散。
+- **皮卡评点**：柯西当年可能正是从分组求和的想法推广到一般非负不增序列的。
 ## 积分估计法
-- 用积分曲线面积近似H_n，因H_n的几何意义是矩形面积，始终大于下方曲边梯形面积，故H_n&gt;∫1/x dx=log x，从而得到H_n&gt;log(n+1)。
-- 皮卡认为这是正规流派，但笔记中内容较多，未详细展开。
-## 差分法（Stolz定理）
-- 通过比较H_n与log n的差分，分子差分（H_{n+1}-H_n=1/(n+1)）和分母差分（log(n+1)-log n=log(1+1/n)）的极限为1，从而证明H_n/log n→1。
-- 皮卡认为此法不自然，因为需要预先知道结果才能选择log n作为比较对象。
+- **核心思路**：用积分曲线的面积近似`hn`，进行放缩。`hn`从几何上可看作一系列高为`1/n`、底为`1`的矩形面积之和，这些矩形始终大于下方曲边梯形的面积。
+- **关键推演**：`∫(1/x)dx = log x`，定积分可通过上下限相减求得，从而给出`hn &gt; log(n+1)`的下界。
+- **皮卡评点**：这是较正规的流派，属于积分收敛估计的方法。
+## 差分法（指数放缩）
+- **核心思路**：对`e^hn`做放缩，利用`e^(1/k) &gt; 1+1/k`的不等式，将指数和转化为连乘积。
+- **关键推演**：`e^hn = ∏e^(1/k) &gt; ∏(1+1/k)`，而`1+1/k = (k+1)/k`，连乘积相邻项相消，最终等于`n+1`。两边取对数即得`hn &gt; log(n+1)`。
+- **皮卡评点**：该证明技巧性强，但本质与积分估计法完全一致，属于后期凑出来的方法——先知道结果再反推，有故弄玄虚之嫌，类似魔术的障眼法。
+## Stolz定理证明
+- **核心思路**：证明`hn`与`log n`是同一增长级别，而`log n`无上界，故`hn`也无上界，级数发散。
+- **关键推演**：利用`Stolz定理`（中文常称`施托尔茨定理`），当分子分母均为无穷大时，可考虑差分`(a(n+1)-an)/(b(n+1)-bn)`的极限。对调和数，分子差分为`1/(n+1)`，分母差分为`log(1+1/n)`，两者求极限为`1`。
+- **皮卡评点**：该证明不自然，属于先射箭后画靶——需要预先知道`hn`与`log n`同阶这一事实，否则无从猜测为何选择`log n`而非`log log n`的平方或`√n`。
 # 核心结论
 ## 核心结论
-- 调和级数∑1/n是发散的，因为其部分和H_n无上界。
-- 柯西凝聚判别法可推广到非负不增序列，其证明思路与分组估计完全一致。
-- 积分估计法证明H_n&gt;log(n+1)，因log函数无上界，故H_n发散。
-- 差分法通过Stolz定理证明H_n/log n→1，从而说明H_n与log n同增长级别，但皮卡认为此法不自然。
+- **调和级数发散**：级数∑1/n（n从1到∞）是发散的，这是高等数学中的经典结论，对学过微积分的大学生而言是简单问题。
+- **收敛的判定标准**：对正向级数，若所有部分和sn都小于某个固定实数a（上界），则级数收敛；反之，若能证明sn大于某个单调递增且无上界的bn，则级数发散。
+- **第一个网友的分组证明**：将调和级数分组——第1项单独一组，1/2+1/3一组，1/4至1/7一组，1/8至1/15一组——每组和都大于1/2，而组数无限多，故部分和无上界，级数发散。
+- **柯西凝聚判别法**：其证明思路与上述分组求和完全一致，适用于非负不增序列；对∑1/n应用该判别法，可转化为判断∑2^k·(1/2^k)=∑1的收敛性，而无穷个1相加显然无上界，故发散。
+- **第二个网友的证明**：证明hn &gt; log(n+1)，因log(n+1)无上界，故hn也无上界，级数发散。
+- **积分估计法**：用积分曲线面积近似hn——调和级数的部分和从几何上可看作矩形面积，始终大于下方曲边梯形面积，即大于∫1/x dx = log x，从而得到hn &gt; log(n+1)的下界。
+- **差分法（指数放缩）**：利用e^(1/k) &gt; 1+1/k，将e^hn展开为连乘积，相邻项相消后得到n+1，从而证明hn &gt; log(n+1)。
+- **Stolz定理证明**：通过比较hn与log n的差分（分子差分为1/(n+1)，分母差分为log(1+1/n)），两者极限为1，故hn/log n的极限为1，log n无上界，hn发散。
 ## 易混点与适用边界
-- 收敛与发散的定义：收敛要求所有部分和小于某个固定上界，发散则要求部分和无界递增。
-- 柯西凝聚判别法仅适用于非负不增序列，不适用于一般级数。
-- 差分法需要预先知道结果（如H_n/log n→1）才能选择比较对象，否则难以自然想到。
-- 积分估计法依赖于微积分知识，而e^{1/k}&gt;1+1/k不等式本身需要微积分证明，但也可用中学知识近似。
+- **收敛与发散的定义**：收敛要求所有部分和sn都小于某个固定上界a（对任意正整数n成立）；发散则要求部分和能超过任意给定的数，两者判定标准不同，不可混淆。
+- **分组证明的适用条件**：分组求和法要求每组和都大于某个固定正数（如1/2），且组数无限多；该方法可推广到一般非负不增序列，即柯西凝聚判别法的适用范围。
+- **柯西凝聚判别法的适用前提**：仅适用于非负不增序列；对增长缓慢、不易直接判断收敛性的级数有本质帮助。
+- **积分估计法的几何前提**：调和级数部分和对应矩形面积始终大于下方曲边梯形面积，这一放缩关系是该方法成立的基础。
+- **差分法的技巧性局限**：e^(1/k) &gt; 1+1/k这一不等式本身需要微积分或极限知识支撑，若未建立极限概念则需额外证明(1+1/k)^k &lt; e；皮卡认为该方法属于「后期凑出来的」，因为需要先知道结果再反推。
+- **Stolz定理证明的不自然之处**：该方法需预先知道hn与log n同阶（即hn/log n极限为1）这一事实，属于「先射箭后画靶」；若不知道hn的变化率，没有理由凭空选择log n作比较对象，也可以蒙log log n的平方或根号n。
+- **log记法的地域差异**：原文指出log在美国写法中即自然对数ln，ln是欧洲经苏联传入中国的记法，两者表示同一函数。
+- **皮卡对技巧性证明的批评**：某些证明（如差分法）本质上是简单事实的障眼法包装，虽让人感觉magic，但实际妨碍理解，属于「故弄玄虚」「装逼」。
 ## 待澄清问题
-- 皮卡提到“dialectic分解”思路，但表示“一时半会也讲不清楚”，留待后续。
-- 皮卡表示“后面还有很多方法，我们有机会再评论”，并计划根据反响决定是否出下一期。</t>
+- **后续内容安排**：皮卡表示调和级数发散性还有很多证明方法，留待后续评论；若本期反响不错，将出下一期，并可能评论网友投稿的解题思路。
+- **Dialectic分解思路**：第一个证明背后还有dialectic分解的思路，皮卡表示「一时半会讲不清楚」，本期未展开。</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>54.4</v>
+        <v>34.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7465/1465</t>
+          <t>7465/3263</t>
         </is>
       </c>
     </row>
@@ -4943,74 +4934,88 @@
       <c r="C15" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本次分享会由工作室老李主讲，围绕GitHub这一全球性开源资源平台展开，核心议题包括两大板块：一是介绍平台上实用、热门的开源项目，二是解决国内用户访问GitHub时常遇到的网络不通、页面全英文、原生搜索不好用等问题。整体逻辑框架为“项目展示—问题解决—技巧演示”，先通过多个具体项目（如工作性价比评估、表情包合集、AI工具等）展示平台价值，再针对访问、汉化、搜索三大痛点逐一给出解决方案，并讲解项目页面的基本结构与判断项目活跃度的方法。分享基调为实用导向，所有提及项目与技巧均整理成文档供观众领取。
+本期视频由工作室老李主讲，围绕GitHub这一开源资源平台，介绍其作为“宝藏资源库”的实用价值，并解决国内用户访问、汉化、搜索与页面使用中的常见问题。整体逻辑框架分四块推进：先推荐一批实用热门项目（如工作性价比评估、表情包博物馆、健康指南、一键证件照、自重健身、教材合集、全自动视频生成、声音克隆、AI学习资源库等）；再针对国内访问困难给出三种解决方案（Watt Toolkit加速软件、镜像站、魔法/VPN）；随后解决全英文页面的汉化问题（推荐谷歌翻译或沉浸式翻译插件）；最后讲解GitHub原生搜索的局限、项目页面各功能（star、watch、fork、about、release、readme、commit日期）及通过explore/trending或ChatGPT等AI工具获取热门项目的方法。整体立场倾向明确：GitHub资源丰富但需掌握访问与使用技巧，推荐以Watt Toolkit或魔法解决访问问题，并建议用AI工具弥补原生搜索的不足。
 # 核心概念
-## GitHub 实用项目
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等，综合评估后给出工作性价比分数和评级；演示中程序员岗位获评「性价比还不错，优质牛马」。
-- **表情包博物馆**：收录国内过去几年全网爆火的表情包大合集，含甄嬛传、罗翔、特朗普、马保国等主题，可用于斗图。
-- **健康活到150岁指南**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态。
-- **一键做证件照项目**：上传大头照即可一键抠图换背景，生成不同标准的证件照和多种规格打印模板。
-- **丐版健身教练项目**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，无需健身器材或真人教练。
-- **教材合集项目**：收集国内所有小学、初中、高中及部分大学的PDF教材，全部免费使用。
-- **全自动视频生成项目**：即 `morning printer Turbo`，近期热门。
-- **声音克隆模型 `ChatBox TTS`**：零样本语音克隆，情感控制到位，克隆声音接近真人；上传自己的音频即可合成指定台词。
-- **AI学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术，作者整理成500多页PDF文档，含大量示意图。
-- **`awesome AI Apps` 项目**：收录大模型最新的Agent应用，如医学影像数据分析Agent、AI投资Agent、竞争对手情报分析Agent等，可用于跟进AI应用落地案例或寻找创业点子。
-## GitHub 访问技巧
-- **Watt Toolkit 加速软件**：进入官网选择适合电脑的版本下载安装，打开后找到网络加速并勾选「GitHub加速」，即可流畅访问。
-- **GitHub 镜像站**：如 `gh-proxy`，浏览器点开即可直接访问GitHub，默认是镜像的项目地址，也可搜索其他项目；速度和稳定性比加速软件差。
-- **VPN（魔法）**：主讲人个人最推荐的方式，需自行注册GitHub账号，用国内QQ邮箱即可注册。
-## GitHub 页面汉化
-- **浏览器翻译插件**：谷歌浏览器推荐 `谷歌翻译` 或 `沉浸式翻译`，安装后可将网页直接翻译成中文，翻译效果基本够用；安装路径为「三个点 → 拓展程序 → 管理拓展程序 → 搜索插件名安装」。
-- **汉化插件**：动手能力强的用户可额外安装，实现更彻底的界面汉化。
-## GitHub 搜索方法
-- **原生搜索**：顶部搜索框输入关键词（如录屏的英文 `screen record`），默认按与搜索词的匹配度排序；更常用的是按 `star` 数排序，star越多代表项目越受欢迎、江湖地位越高。
-- **原生搜索的局限**：按搜索词精准匹配，如搜 `screen record` 与 `screen recording` 按星标排序结果不同，导致英文不好时搜得不够准确、全面。
-- **AI 搜索（推荐）**：在ChatGPT中用中文提问（如「在GitHub上帮我找好用的录屏软件」），AI可搜齐热门工具并总结成表格，弥补精准匹配的不足。
-## GitHub 项目页面结构
-- **项目本质**：GitHub上的一个项目本质上是一个文件夹，项目名字下面是子文件夹或文件。
-- **`watch` / `fork` / `star`**：分别对应关注项目、复制项目到自己的账号、收藏和点赞（一键三连）。
-- **`About` 简介**：项目右侧的一句话简介，说明项目是干什么的。
-- **`Release` 安装包**：存放软件的安装包，点开可看到最新版本并下载安装。
-- **`Readme` 文件**：项目的说明书，默认在项目最下面展开显示，用于了解项目用途、安装使用方法，是了解一个项目必看的内容。
-- **`commit` 日期**：每个文件最近的提交日期即最近更新时间；若更新日期是好几年前，大概率是无人维护的僵尸项目。
-- **`Explore` → `Trending`**：可查看全站当天、本周、本月最热门的项目，适合跟踪最新热门开源项目。
-- **AI 获取热门项目**：让ChatGPT找 `GitHub daily`，可及时分享各种最新最热门的项目。
+## 工作性价比评估项目
+- 输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等参数，综合输出工作性价比分数与评级。
+- 老李用自己之前的程序员工作测试，评估结果为「性价比还不错，优质牛马」。
+## 表情包博物馆
+- 收录国内过去数年全网爆火的表情包大合集，涵盖甄嬛传、罗翔、特朗普、马保国等主题。
+- 老李评价：斗图用这个项目「可以把对方按在地上摩擦」。
+## 健康指南项目
+- 分享经科学验证的健康知识，如间歇性进食可促进胆汁代谢、炎症自愈，吃天然发酵类食品可改善肠道菌群生态。
+- 老李表示不指望活到150岁，只希望教程能帮自己活到领养老金那天。
+## 一键做证件照项目
+- 上传一张大头照即可一键抠图换背景，生成不同标准的证件照和各种规格的打印模板。
+## 自重健身项目
+- 选择要练习的肌肉群（如腹肌）后，提供用身体自重练习的参考动画，可跟着做。
+- 老李评价：适合请不起真人教练的人，是「丐版健身教练」。
+## 教材合集项目
+- 收集国内所有小学、初中、高中及部分大学的PDF教材，全部免费使用。
+## 全自动视频生成项目 Morning Printer Turbo
+- 近期热门项目，支持全自动视频生成。
+## 声音克隆模型 ChatBox TTS
+- 零样本语音克隆，情感控制到位，克隆声音像真人说话；上传自己的音频即可合成指定台词。
+## AI学习资源库
+- 涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术教程，作者整理成500多页PDF文档，含大量示意图。
+## Awesome LLM Apps
+- 收录大模型最新Agent应用，如医学影像数据分析、AI投资、竞争对手情报分析等。
+- 老李建议：跟进AI应用落地案例或找创业点子可看此项目。
+## GitHub访问加速方法
+- 方法一：使用Watt Toolkit加速软件，进入官网选择适合电脑的版本下载安装，打开后找到网络加速勾选GitHub加速即可流畅访问。
+- 方法二：使用GitHub镜像站（如gh-proxy），浏览器直接打开即可访问，也可搜索其他项目。
+- 方法三：使用魔法（VPN），老李个人最推荐。
+- 老李比较：Watt Toolkit更流畅，镜像站速度和稳定性较差。
+## GitHub页面汉化
+- 推荐谷歌浏览器安装谷歌翻译或沉浸式翻译插件，安装方法为点击浏览器右上角三个点→扩展程序→管理扩展程序→搜索插件名安装。
+- 翻译效果基本够用；动手能力强的还可安装汉化插件。
+## GitHub原生搜索与AI搜索
+- 原生搜索按搜索词精准匹配，如搜screen record和screen recording按星标排序结果不同，对国人不好用。
+- 推荐用ChatGPT等AI工具搜索，用中文提问即可找到热门项目并总结成表格，结果更全面。
+## GitHub项目页面功能
+- star相当于收藏和点赞，watch是关注项目，fork是复制项目到自己的账号。
+- about是项目简介，release是软件安装包，readme是项目说明书（默认在项目最下面展开显示）。
+- commit日期即最近更新时间，若更新日期是好几年前，大概率是没人维护的僵尸项目。
+- 左侧explore中的trending可查看全站当天、本周、本月最热门项目；也可让ChatGPT帮忙找GitHub daily获取最新热门项目。
 # 核心结论
 ## 核心结论
-- **GitHub 定位**：GitHub 不只是代码托管平台，而是几乎能找到资源、教程、工具的巨大宝藏资源库，包含名校公开课（麻省理工、斯坦福）、大厂面试题与面试经验（字节、阿里、腾讯）、大公司最新开源大模型（Google、阿里）、AI 副业教程等正经内容，以及表情包合集、养生指南、大厂黑名单等非正经内容。
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事评价等因素，综合给出工作性价比分数和评级；主讲人测试其程序员工作，评估结果为「性价比还不错，优质牛马」。
-- **表情包博物馆项目**：收录国内过去几年全网爆火的表情包大合集，含甄嬛传、罗翔、特朗普、马保国等主题。
-- **健康活到 150 岁指南项目**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态。
-- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照和多种规格打印模板。
-- **健身教练项目**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，适合请不起真人教练的用户。
-- **教材合集项目**：收集国内所有小学、初中、高中及部分大学 PDF 教材，全部免费。
-- **全自动视频生成项目**：即 Morning Printer Turbo，为近期热门项目。
-- **声音克隆模型 ChatBox TTS**：零样本语音克隆，情感控制到位，克隆声音像真人说话；上传自己的音频可合成英文台词。
-- **AI 学习资源库项目**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
-- **Awesome AI Apps 项目**：收录大模型最新 Agent 应用，如医学影像数据分析 Agent、AI 投资 Agent、竞争对手情报分析 Agent，可用于跟进 AI 应用落地案例或寻找创业点子。
-- **GitHub 访问方案**：国内访问 GitHub 又卡又难，提供三种方法——Watt Toolkit 加速软件（进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选 GitHub 加速）、GitHub 镜像站（如 gh-proxy，浏览器点开直接访问，可搜索 GitHub 其他项目）、VPN（魔法，主讲人个人最推荐）。
-- **页面汉化方案**：给浏览器安装翻译插件，谷歌浏览器推荐谷歌翻译或沉浸式翻译，可将网页翻译成中文；动手能力强的可安装汉化插件。
-- **GitHub 搜索方法**：原生搜索按搜索词精准匹配排序，如搜 screen record 和 screen recording 按星标排序结果不同；推荐用 ChatGPT 等 AI 搜索，用中文提问即可汇总热门录屏工具并总结成表格。
-- **项目页面结构**：GitHub 项目本质是文件夹，项目名字下面是子文件夹或文件；Watch 是关注项目，Fork 是复制项目到自己的账号，Star 相当于收藏和点赞；About 是项目简介；Release 是软件安装包，可下载最新版本。
-- **Readme 文件**：是项目说明书，默认在项目最下面展开显示，可了解项目用途、安装使用方法，是了解项目必看的内容。
-- **项目维护判断**：通过每个文件最近的 commit 日期判断，可理解为最近更新时间；更新日期是好几年前的，大概率是没人维护的僵尸项目。
-- **热门项目追踪**：点开左侧 Explore 的 Trending，可查看全站当天、本周、本月最热门项目；也可让 ChatGPT 找 GitHub daily，及时分享最新最热门项目。
+- **GitHub 定位**：不只是代码托管平台，而是几乎能找到资源、教程、工具、开源大模型、AI 学习资料、面试题与经验等内容的宝藏资源库，也包含表情包合集、养生指南、大厂黑名单等非正经内容。
+- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等，输出工作性价比分数与评级；老李测试其程序员工作，评估结果为「性价比还不错，优质牛马」。
+- **表情包博物馆项目**：收录国内过去数年全网爆火的表情包大合集，含甄嬛传、罗翔、特朗普、马保国等主题。
+- **健康指南项目**：分享经科学验证的健康知识，如间歇性进食可促进胆汁代谢、炎症自愈，吃天然发酵类食品可改善肠道菌群生态。
+- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准的证件照与各种规格打印模板。
+- **自重健身项目**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，适合请不起真人教练的用户。
+- **教材合集项目**：收集国内所有小学、初中、高中及部分大学的 PDF 教材，全部免费。
+- **全自动视频生成项目**：Morning Printer Turbo，近期热门。
+- **声音克隆模型 ChatBox TTS**：零样本语音克隆，情感控制到位，克隆声音接近真人；演示上传本人音频合成英文台词。
+- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
+- **Awesome LLM Apps 项目**：收录大模型最新 agent 应用，如医学影像数据分析、AI 投资、竞争对手情报分析等 agent，可用于跟进 AI 应用落地案例或寻找创业点子。
+- **GitHub 访问方案**：方法一用 Watt Toolkit 加速软件（进入官网选对应版本下载安装，打开后找到网络加速勾选 GitHub 加速），对多数人更流畅；方法二用镜像站如 gh-proxy（浏览器直接访问，可搜索其他项目），速度与稳定性较差；方法三用魔法（VPN），老李个人最推荐。
+- **GitHub 注册**：注册简单，用国内 QQ 邮箱即可。
+- **页面汉化方案**：给浏览器装翻译插件，谷歌浏览器推荐谷歌翻译或沉浸式翻译，安装路径为「三个点 → 扩展程序 → 管理扩展程序 → 搜索插件名安装」，翻译效果基本够用。
+- **原生搜索局限**：GitHub 原生搜索按搜索词精准匹配，如搜 screen record 与 screen recording 按星标排序结果不同，对国人不好用。
+- **AI 辅助搜索**：推荐用 ChatGPT 等 AI 工具，用中文描述需求（如「在 GitHub 上帮我找好用的录屏软件」），可找齐热门项目并总结成表格，能覆盖原生搜索漏掉的项目。
+- **项目页面功能**：star 相当于收藏和点赞，watch 是关注项目，fork 是复制项目到自己的账号；about 为项目简介；release 为软件安装包，可下载最新版本；readme 是项目说明书，默认在项目最下面展开显示，是了解项目必看内容。
+- **项目活跃度判断**：每个文件有最近 commit 日期（即最近更新时间），若更新日期是好几年前，大概率是没人维护的僵尸项目。
+- **热门项目追踪**：点开左侧 explore 中的 trending，可查看全站当天、本周、本月最热门项目；也可让 ChatGPT 等工具帮忙找 GitHub daily，及时分享最新最热门项目。
 ## 易混点与适用边界
-- **三种访问方式对比**：Watt Toolkit 加速软件对大多数人更流畅；镜像站速度和稳定性更差；VPN（魔法）为主讲人个人最推荐，但需自行解决获取方式。
-- **GitHub 原生搜索局限**：按精准匹配排序，同一含义的不同英文表达（如 screen record 与 screen recording）搜索结果不同，对英文不好、搜索内容不准确不全面的用户不友好。
-- **Star 数与项目质量**：Star 数代表项目受欢迎程度（江湖地位），Star 越多项目越受欢迎，但原文未说明 Star 数与项目质量直接等同。
-- **commit 日期判断**：commit 日期可理解为最近更新时间，多年未更新大概率是僵尸项目，但原文未给出具体年限标准。
-- **镜像站使用限制**：默认是镜像的项目地址，但搜索 GitHub 其他项目没有问题。
-- **GitHub 注册**：注册很简单，用国内 QQ 邮箱就可以。</t>
+- **Watt Toolkit 与镜像站对比**：Watt Toolkit 更流畅，镜像站（如 gh-proxy）速度与稳定性更差；老李个人最推荐魔法（VPN）方式。
+- **原生搜索与 AI 搜索对比**：原生搜索按关键词精准匹配，结果不全面（同一工具因用词不同可能搜不到）；AI 搜索用中文描述即可，结果更全面并自动总结成表格。
+- **star、watch、fork 的区别**：star 是收藏和点赞，watch 是关注项目，fork 是复制项目到自己的账号，三者功能不同。
+- **readme 与 about 的区别**：about 是项目的一句话简介，readme 是详细的项目说明书（含怎么安装使用），默认在项目最下面展开显示。
+- **commit 日期的判断边界**：更新日期是好几年前，大概率是没人维护的僵尸项目；更新日期较新则项目仍在维护。
+- **镜像站使用边界**：默认打开的是镜像的项目地址，但搜索 GitHub 其他项目没有问题。
+- **翻译插件适用性**：推荐用于谷歌浏览器，谷歌翻译或沉浸式翻译两个插件装好后可直接把网页翻译成中文，翻译效果基本够用。
+## 待澄清问题
+未提及</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>39.1</v>
+        <v>44.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4014/4076</t>
+          <t>4014/3915</t>
         </is>
       </c>
     </row>
@@ -5381,68 +5386,72 @@
       <c r="C16" t="inlineStr">
         <is>
           <t># 访谈概述
-本期《锵锵三人行》围绕日本历史剧《大奥》与明朝历史展开，主持人窦文涛与嘉宾马未都、《明朝那些事儿》作者当年明月（石悦）等对谈，对比中日文化差异，并延伸至明朝历史特点与历史研究难点。关于《大奥》，嘉宾认为它是《大长今》之后最有影响的外国电视剧，其历史背景对应中国晚明到清初及明治维新前；讨论指出日本文化体现极端精神，所有事情做到尽头，与中国的“中庸”文化形成鲜明对比，日本社会鄙视投机取巧，终身雇佣制下跳槽率最低，民族重视死亡，经济危机时身家万贯者剖腹自杀。关于明朝历史，当年明月表示明史资料最多，但同一事件可能有7个不同说法；朱元璋从乞丐当上皇帝，独此一份，定下明朝规章制度基本无大改动；明末市民生活轻松，江浙工商业兴起，三言二拍等娱乐产品出现；1644年明朝灭亡时北京闹瘟疫（疙瘩瘟，可能为天花）。关于明朝皇帝，讨论涉及明武宗正德要去江南被大臣跪金水桥抗议、打死十几人仍不让去，正德到扬州要东西政府不给、让人把酒席折成银两带回；天启帝爱当木匠，干完活让大臣去卖，卖得好有成就感。嘉宾认为正德皇帝被评价为最荒淫可能因嘉靖非其亲生，编史有偏颇。
+本期《锵锵三人行》围绕日本历史剧《大奥》与《明朝那些事儿》展开中日文化差异及明朝历史的漫谈。受访者包括《明朝那些事儿》作者当年明月（发言者2）及嘉宾马先生（发言者3）等，主持人（发言者1）引导话题。节目先由《大奥》热播切入，讨论日本文化中的极端精神、忠诚文化与严谨态度，并与中国的中庸文化作对比；随后转向明朝历史，探讨明史研究难点、朱元璋的推崇、明朝兴亡经验教训及明式家具等话题。受访者核心观点包括：日本文化讲究“所有的事情要做到尽头”的极端精神，战后仅用30年成为世界第二经济强国（绝对量）；中国历史“从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”；明末江南市民生活轻松富足，李自成起义源于陕西大规模灾荒。访谈看点在于当年明月提出明史“一个事件可能有7个不同的说法”的研究难点，以及正德皇帝被嘉靖时期史官抹黑、天启皇帝爱当木匠等独家历史解读。
 # 访谈详细记录
-## 日本历史剧《大奥》与日本文化
-- **《大奥》反响**：发言者1引出刚播完并引起很大反响的《大奥》，发言者3认为它是《大长今》以后最有影响的外国电视剧，发言者2表示赞同。
-- **《大奥》历史背景**：发言者3介绍该剧三部曲，前两部对应中国晚明到清初时段，发言者2补充后一部在明治维新之前，是一部有跨越性的历史剧。
-- **大奥含义**：发言者3解释大奥即普通话的后宫，日语中「奥」指很深的地方、屋子最里处，发言者2补充另一层意思是一般人不准进去。
-- **大奥的规矩**：发言者3指出大奥定下非常严谨的规矩，包括后宫不许进人；发言者1描述将军出场时所有人呈45度鞠躬、依次鞠躬的场面华丽。
-- **幕府将军与天皇关系**：发言者2说明天皇一直是摆设，实际权力在幕府将军，德川家康开创德川幕府后权力集中在一人手上；天皇曾因想举办活动没钱找将军要钱被拒，后以退位抗议。
-- **日本极端精神**：发言者2认为从《大奥》可看出日本文化从头到尾没变，是一种极端精神，所有事情要做到尽头；发言者3补充它是发自内心的，与中国人不同。
-- **战后经济成就**：发言者3指出日本1945年战后用30年时间成为世界第二经济强国，以绝对量计，是强国中唯一没有资源的国家。
-## 中日文化差异与日本民族精神
-- **中国中庸与日本极端**：发言者2对比中国中庸文化与日本极端精神，以家具店硬木刻云彩为例，说明中国讲究融合、走最适合的路；日本则坚持一个原则，如炮手开炮时忘记一切只记得把炮开出去即达最高境界。
-- **日本忠诚文化**：发言者3认为日本是忠诚文化的典型国度，忠诚靠具体事例体现而非说教，如《大奥》中阿福25岁进大奥当奶妈、65岁去世，40年完全出于公心做事。
-- **终身雇佣制**：发言者2指出日本跳槽率最低，终身雇佣制下缺乏竞争却仍保持高积极性，是西方经济学家不能理解的经济学奇迹。
-- **投机取巧无生存环境**：发言者3认为日本投机取巧的人没有生存环境，社会文化的鄙视非常难过；举例日本做绳子做到全日本第一的人，几年不赚钱铺市场，最终通过两边各加2%获利。
-- **日本重视死亡**：发言者2认为日本民族有寻死的潜在欲望，因岛国生存条件恶劣而对死亡不惧怕甚至有点向往；发言者3修正为日本民族不是藐视生命而是重视死亡，经济危机时身家万贯者剖腹自杀。
-- **日本豆腐厂见闻**：发言者3讲述参观日本最底层工厂，豆腐厂规定当天做当天卖，所有人夜里11:45坐好等钟，12点整一起开始工作，到四点多干完上市，无人闲聊。
-## 明朝历史与《明朝那些事》
-- **《明朝那些事》发行**：发言者3指出该书发行量排行第一，各报文学类都是第一。
-- **写明史的原因**：发言者2解释写明史因明史资料最多，历史研究有两个难点：先秦春秋没史料，明清史料太多但同一事件可能有7个不同说法，如罗生门。
-- **明朝历史特点**：发言者3指出明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变、夺门之变，皇上被瓦剌军抓起来又扶弟弟上位，构成现代版电视剧情节。
-- **朱元璋评价**：发言者2认为朱元璋从乞丐当上皇帝独此一份，刘邦好歹是亭长；朱元璋定下明朝规章制度基本无大改动，是了不起的人才；发言者3认为人的因素最大，改变时势一定出现一个人。
-- **朱元璋参加起义**：发言者2讲述朱元璋因送信被人告发，没办法只能去参加起义军，当年造反是要掉脑袋的风险事。
-- **明末市民生活**：发言者2指出明末很多真相被掩盖，市民生活轻松舒服，想去哪去哪，江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍等娱乐产品出现说明有养活自己的资本；李自成起义因陕西大规模灾荒。
-- **明末艺术**：发言者3指出明末工艺变得非常精细，日本派大量工匠来交流学习；文征明、唐寅、董其昌都是那个时期的人，画的是小桥流水，而八大山人画翻白眼是对社会愤愤不平。
-- **历史经验教训**：发言者2提出「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因历史事件发生时有背景，史书记载只是照片，而古人的生活是录像，不能套用经验。
-- **1644年北京瘟疫**：发言者2提到1644年明朝灭亡那年北京闹瘟疫，叫疙瘩瘟，今天看就是天花，曾与老师王佩奇交流认为明朝亡得蹊跷。
-- **王朝300年大限**：发言者3指出中国历史王朝300年是大限，跨过300年的只有宋朝（南北宋接上，退让大半个国土延续319年），汉朝中间隔断14年，唐朝明朝清朝都没跨过。
-## 明朝皇帝趣事与历史评价
-- **明武宗去江南**：发言者2讲述正德皇帝要去江南，大臣全跪金水桥前抗议，皇帝气坏了到锦衣卫打死十几人还是不让去。
-- **正德打秋风**：发言者2讲述正德到扬州要东西，政府说没有，皇帝不生气，让人准备酒席后说吃不了，把酒席折合成银两带回去。
-- **天启帝当木匠**：发言者3讲述天启帝干完活差大臣去卖，回来打听卖得怎么样，卖得很好成就感特大；发言者4调侃要是亲自去卖更好卖。
-- **正德被写坏的推测**：发言者2认为正德皇帝被评价为最荒淫可能因嘉靖非其亲生而是堂兄弟，嘉靖指派杨廷和等人编《明武宗实录》有偏颇；正德从江南回来在通州先停半天，派人打探京城有无埋伏，显示很有城府。
-- **正德豹房**：发言者2解释豹房其实是玩的地方，有动物园养了豹子，也有女人，但后宫也是女人，不影响其他问题。
-- **正德无后**：发言者3指出正德是明朝定论最荒淫的皇帝，没少找女人但不留种，没有生育能力，到嘉靖这拐弯。
-- **正德对宫廷外女人有兴趣**：发言者3认为正德对宫廷内女人没兴趣因禁忌太多，发言者4补充宫廷女人被训练过、太保守，民女不知他是谁所以不一样。
-- **明式家具地位**：发言者3指出天启帝当木匠从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然，皇帝下大力气做可见影响之深。
+## 日本历史剧《大奥》与文化差异
+- **《大奥》热播反响**：发言者3认为《大奥》是继《大长今》以后最有影响的外国电视剧，发言者2表示赞同，认为确实是一部拍得非常好的作品。
+- **剧情时代背景**：发言者3指出《大奥》三部曲中前两部大致相当于中国的晚明到清初时段，发言者2补充还有一部在明治维新之前，是一部有跨越性的历史剧。
+- **严谨精神**：发言者2认为《大奥》吸引他的是严谨精神，指出回头看《三国演义》会看到群众演员笑，但日本历史剧看不到笑，每个人都特别有专业精神。
+- **大奥含义与规矩**：发言者3解释大奥即普通话的后宫，日语中「奥」指屋子最里处，如「深入堂奥」「道理深奥」；当时已定下非常严谨的规矩，包括后宫不许进人。
+- **幕府将军与天皇关系**：发言者2指出日本天皇一直是摆设，实际权力掌握在幕府将军手中；德川家康开创德川幕府后权力集于一人。受访者认为天皇一点都不崇拜幕府将军，举例天皇想办活动没钱找将军要，将军不给，活动没办成，天皇后来以退位抗议。
+- **日本极端精神**：发言者2认为从《大奥》可看出日本文化从头到尾没变，是一种「极端精神」，特点是把所有事情做到尽头；发言者3认为这是每个人发自内心的，与中国人不同。
+- **战后经济成就**：发言者3指出日本1945年战后用30年时间成为世界第二经济强国（绝对量，非人均量），是世界上强国里唯一没有资源的国家，这不是偶然而是必然，源于全民族的极端精神。
+- **中日文化对比**：发言者2对比中国中庸精神与日本极端精神，举例在家具店看到硬木刻云彩，认为中国讲究融合、走最适合的路；日本则坚持一个原则，如炮手开炮时忘记一切只记得把炮开出去即达最高境界。
+- **忠诚文化**：发言者3认为日本是忠诚文化的典型国度，日本人跳槽率最低，每一次跳槽都是社会资源浪费；发言者2补充日本终身雇佣制下员工积极性仍高，西方经济学家难以理解这一经济学奇迹。
+- **《大奥》剧情体现忠诚**：发言者1复述剧情：女人本有情人发誓救她，将军死后情人放火来救，但女人不跟走，因将军生前说每个人在职位上都能发光发热，她甚至落发出家；发言者3认为这是日本忠诚文化的具体体现，靠具体事例而非说教。
+- **阿福事例**：发言者3提到《大奥》第一集中阿福25岁进大奥当奶妈，65岁去世，40年做事完全出于公心、不夹杂私利，所有人最终都认为她是楷模。
+- **慢慢来才是最快**：发言者2引用他人观点「慢慢来才是最快的方法」，认为所有人按自己角色做事最节省成本，不会互相抵消，形成合力非常可怕。
+- **豆腐厂事例**：发言者3讲述参观日本最底层豆腐厂：规定当天做当天卖，夜里11:45所有人坐好看着表，12点整一起站起来开始工作，到四点多干完上市，没人闲聊胡侃。
+- **岛国生存环境**：发言者2分析日本是岛国，没有资源、常火山地震，跑都没地方跑，人对世界有极强求生欲望或悲观感，必须融入团体按固定规则做事才能生存。
+- **投机取巧无生存环境**：发言者3认为日本投机取巧的人没有生存环境，社会文化鄙视非常难过；举例做绳子做到全日本第一的人几年不赚钱铺市场，之后向两边各要2%利润，靠4%赚大钱。
+- **是否愿做日本人**：发言者3表示在这种文化中愿意也做不成，文化不允许；发言者2表示很不愿意，因日本人很多时候盲从，且有寻死的潜在欲望。
+- **死亡观**：发言者2认为日本人看樱花只看落的那天，因生存条件恶劣，对死亡不是藐视而是有点向往、不惧怕，二战日军暴行是藐视生命的行为；发言者3不同意，认为日本民族不是藐视生命而是重视死亡，经济危机时很多身家万贯的人剖腹自杀。
+## 明朝历史与《明朝那些事儿》
+- **为何写明史**：发言者2回应为何写明朝而非其他朝代：因为明史资料最多、他最熟。历史研究有两个难点：先秦春秋没史料，史记就那么一两篇都是编的；明清史料堆得比山还高但一个事件可能有7个不同说法，如同黑泽明电影《罗生门》。
+- **明朝历史跌宕起伏**：发言者3指出明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变皇帝被瓦剌军抓走，哥几个又把弟弟扶起来，完全构成现代版电视剧情节。
+- **推崇朱元璋**：发言者2认为朱元璋从乞丐到推翻元朝当皇帝，定下明朝规章制度且基本没有太大改动，是了不起的人才；发言者3补充历史上最底层的人坐到最上面独此一份，刘邦好歹是村长或乡长。
+- **朱元璋起义是逼上梁山**：发言者1提到朱元璋好友汤和让他参加起义军，他在庙里犹豫怕被杀头，后因送信被告发没办法才去；发言者2强调历史最重要的是弄明白这事是真的，旁观者觉得好玩，但当年造反是要掉脑袋的，对他而言非常有风险。
+- **英雄史观**：发言者3认为人的因素最大，改变时势一定是出现一个人；发言者2以《亮剑》李云龙为例，认为朱元璋天分相当高，像会打仗的人打仗，是战场上积累经验的天赋。
+- **明朝经验体现**：发言者3认为明朝经验能体现出来，如仁宣盛世，晚明尽管史书说政治黑暗、皇帝不上朝，但老百姓生活很好；发言者2补充明末市民生活特别轻松舒服，想去哪去哪，江浙一带工商业兴起，给人当雇工活得很滋润，《三言二拍》这类娱乐产品出现说明有养活自己的资本。
+- **李自成起义原因**：发言者2指出李自成起义是因为陕西一带发生大规模灾荒。
+- **明末艺术繁荣**：发言者3提到明末工艺变得非常精细，日本派大量工匠来中国交流学习；文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水，八大山人明末画的都是翻白眼，因对社会愤愤不平。
+- **历史教训**：发言者2引用名言「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，认为历史事件发生时有背景，史书记载只是照片，古人的生活是录像，不能套用经验否则一定倒霉。
+- **明朝有趣之处**：发言者2指出明代宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣），什么都能发生，皇帝出去了还能回来做皇帝。
+- **明朝灭亡蹊跷**：发言者2提到吴三桂与满清合作入关是为崇祯皇帝复仇；1644年李自成军打到京城无人抵抗，因北京闹瘟疫叫疙瘩瘟（即天花）；他与老师王佩奇交流认为明朝亡得真蹊跷，什么坏事衰事都赶上了。
+- **王朝300年大限**：发言者3指出中国历史王朝300年是大限，逼近300年就完了；严格讲跨过300年的只有宋朝（南北宋接上，319年），汉朝中间隔断14年，唐朝明朝清朝都没跨过；发言者2比喻公司成立200多年够本了，明朝几千万人的大摊子能撑276年很不容易。
+## 明朝皇帝趣事与明式家具
+- **明武宗被限制出行**：发言者2讲述正德皇帝要去江南，大臣全跪金水桥前抗议，皇帝气坏了到锦衣卫打死了十几个人还是不让去；后来打服了一批人去了扬州，要东西政府说没有，皇帝不生气，让人准备酒席后折合成银两带回去。
+- **正德皇帝被抹黑**：发言者2分析正德皇帝被写得很差的原因：接班的嘉靖不是他亲生，是堂兄弟，嘉靖指派杨廷和等人编明武宗实录，有偏颇；嘉靖上台搞大礼仪事件为给自己父亲争名分死了很多人。受访者认为正德皇帝绝不是史料写的那么蠢，举例他从江南回来在通州先停半天派人打探京城有无埋伏，很有城府。
+- **豹房真相**：发言者2解释豹房其实是玩的地方，有动物园养了豹子，有女人但后宫也是女人，不影响其他问题；发言者1险些把豹房听成炮房。
+- **正德无后**：发言者3指出正德皇帝是明朝最荒淫的皇帝，没少找女人但不留种，没有生育能力；对宫廷外女人有兴趣，因宫内女人禁忌太多、太保守。
+- **天启皇帝当木匠**：发言者3提到天启皇帝爱当木匠，干完活差大臣去卖，回来还打听卖得怎么样，卖得很好成就感特大；发言者4调侃要是亲自去卖更好卖。
+- **明式家具地位**：发言者3认为天启皇帝当木匠从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然，所有偶然中一定有必然因素。
+- **明清朝审美差异**：发言者3指出宋明是典型汉人文人政权，审美判断不是表象的；满族是异族，对美的判断是表象的。今天外在美直观能看到的都卖得贵，但晚清到民国初年收藏中这种东西不值钱，一定是素雅的。
 # 关键引语与金句
-&gt; 慢慢来才是最快的方法。
-- 回应如何理解日本文化中按角色行事、不夹杂个人小聪明的思维方式。
-&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-- 回应明朝兴亡能否体现历史经验教训的问题。
-&gt; 历史它那个事儿发生的时候是有背景的……你不比前人聪明，你甚至可能比前人笨，当那种情况出现的时候，你也得那么办。
-- 解释为何不能简单套用历史经验教训。
-&gt; 史书上记载下来的是什么？照片。我们实际的生活，古人的生活都是录像。
-- 说明史书记载与真实历史之间的差距，回应为何很多人对历史有误解。
-&gt; 日本的文化跟中国的文化存在一个极大的不同……中国的文化精神是什么？是中庸。
-- 对比中日文化差异，以马未都家具店中硬木刻云彩为例说明中庸之道。
-&gt; 日本人的这种极端精神，使一个国家在战后这样一个不利的局面下，只需要30年的时间它进入世界第二经济强国。
-- 回应日本战后经济崛起的原因，强调其全民族极端精神的作用。
-&gt; 日本民族它不是藐视生命，它是重视死亡，它是翻着的。
-- 回应发言者2关于日本藐视生命的说法，以经济危机时身家万贯者剖腹自杀为例。
-&gt; 一个人到战场上死生多少年没死，最后积累下来经验，然后我一上战场我就知道敌人会往哪走，我该怎么打。天赋。
-- 以《亮剑》中李云龙为例，解释朱元璋这类人物的军事天赋。</t>
+&gt; “慢慢来才是最快的方法。”
+- 背景：发言者2在讨论日本文化中人人按角色行事、不夹杂个人小聪明时，引述他人观点说明按部就班反而最有效率。
+&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
+- 背景：发言者2回应明朝兴亡经验教训能否被后世吸取时，总结历史教训难以真正被借鉴。
+&gt; “历史它那个事儿发生的时候是有背景的……当那种情况出现的时候，你也得那么办。”
+- 背景：发言者2解释为何不能简单从历史中套用经验教训，强调后人并不比前人聪明，须理解历史事件发生的具体背景。
+&gt; “史书上记载下来是什么。照片……古人的生活都是录像。”
+- 背景：发言者2用照片与录像作比，说明史书记录只是瞬间定格，后人看不到事件前后的完整脉络，因此容易误解历史。
+&gt; “日本的文化跟中国的文化存在一个极大的不同……中国的文化精神是什么？是中庸。”
+- 背景：发言者2对比中日文化差异时，以马先生家具店中硬木刻云彩为例，阐释中国中庸精神与日本极端精神之别。
+&gt; “所有人按照自己的角色去做自己的事情，最节省成本了……大家都会有一个共同的目标往前走。”
+- 背景：发言者2分析日本终身雇佣制下员工积极性为何仍高，认为各守本分形成合力是日本社会高效运转的原因。
+&gt; “日本呢它是一岛国……没有资源，什么都没有，还经常火山地震……人本身呢对这个世界他有一种极强的那种求生欲望。”
+- 背景：发言者2解释日本民族集体主义与极端精神的成因，认为恶劣的生存环境迫使日本人必须融入团体、按规则行事以求生存。
+&gt; “他藐视生命，他很多人表示你为什么说二战时候日军到中国会有那么多暴行，它是一种藐视生命的行为。”
+- 背景：发言者2回应日本文化中对死亡的态度时，指出日军侵华暴行与日本民族藐视生命的倾向有关。</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>61.4</v>
+        <v>73.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14719/3519</t>
+          <t>14719/4542</t>
         </is>
       </c>
     </row>
@@ -5779,38 +5788,41 @@
       <c r="C17" t="inlineStr">
         <is>
           <t># 就诊概况
-48岁男性患者张学恒，在成都轻工研究所从事科研工作，因上腹反复疼痛4年、近3个月发作频繁，于消化专科就诊。医生初步了解病情后，建议留大便检查并预约胃镜检查，以明确有无消化道出血及进一步诊治。
+48岁男性患者张学恒，职业为科研工作（成都轻工研究所），因上腹反复疼痛4年、近3个月加重就诊于消化专科，为初诊。患者主诉心窝部烧灼样疼痛，进食冷硬食物或工作紧张时诱发，近3个月疼痛可忍受，无夜间痛醒；近4年出现两次黑便（1年前、3个月前），每次持续约1个月，两次均住院诊断为大便出血；近2个月呕吐数次，吐出黄水样酸味物。既往有甲肝病史（已愈）、磺胺药过敏史；近期服用奥美拉唑（武汉药厂产）和阿莫西林，效果不佳。初步考虑消化系统疾病，需进一步检查明确，已预约胃镜。
 # 病史与背景
-- **现病史**：上腹疼痛4年，每年春季多发，近3个月反复发作；疼痛位于心窝部，呈烧灼感，冷食、硬食、辛辣及工作紧张时诱发，无夜间痛醒，疼痛可忍受。
-  - 一年前及三个月前各出现一次黑便，每次持续约一个月，每日最多两次，大便形状基本正常，仅颜色改变；两次均住院治疗，住院后大便转黄。
-  - 近两个月呕吐数次，吐出酸味黄水样物，含未消化食物，多在晚上感觉胀时吐出。
-- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；无手术史。
-- **过敏史**：小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手出现红疹，持续半个月，确诊磺胺药过敏，此后不能服用磺胺药。
-- **家族史**：父亲76岁，有低血压；母亲75岁，有冠心病；婶婶（叔叔的爱人）有胃癌，患者担心自己是否患胃癌。
-- **个人史**：成都人，在成都轻工研究所从事科研工作，工作紧张，经常加班熬夜；吸烟史，以前每天一包，现限制在10支以内；偶尔饮酒，平时不喝；喝茶，一天泡两次。
-- **近期用药**：近期服用奥美拉唑、阿莫西林及医务室配制的胃炎合剂，效果不佳。
+- **现病史**：上腹疼痛4年，每年春季多发，近3个月持续；疼痛位于心窝部，有烧灼感，进食冷硬食物或工作紧张时诱发，暖和、工作轻松时无痛；近3个月疼痛可忍受，无夜间痛醒。
+- **黑便史**：近4年出现两次黑便，分别于1年前和3个月前，每次持续约1个月，每日最多2次，大便性状正常仅颜色改变；两次均住院检查诊断为大便出血，住院2-3天后大便转黄。
+- **呕吐**：近2个月呕吐数次，吐出黄水样酸味物，含早中餐食物，晚间腹胀时呕吐后缓解。
+- **既往史**：16岁时患甲肝，在三医院住院1个月，出院后肝功能正常；小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手出现红疹，持续半个月，确诊磺胺过敏。
+- **个人史**：双眼近视400度，偶有口腔溃疡；吸烟史，以前每天1包，现限制在10支以内；饮酒少量，平时不喝；工作紧张，经常加班熬夜。
+- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；婶婶（无血缘关系）患胃癌。
+- **近期用药**：近期服用奥美拉唑（武汉药厂产）和阿莫西林，效果不佳，现每日4-5次；有时服用医务室自配胃炎合剂。
 # 诊断与检查结果
-医生初步判断患者病情与工作紧张、饮食刺激有关，建议进一步检查以明确诊断。患者有两次黑便史，需明确有无消化道出血；有胃癌家族史（婶婶），虽无血缘关系，但患者有担忧。
+尚未确诊，需进一步检查明确。患者有两次黑便史，需排查消化道出血；医生建议留大便检查，并预约胃镜。患者担心是否患胃癌，医生解释婶婶（无血缘关系）的胃癌与患者无直接关联，但需进一步检查。
 # 治疗方案与医嘱
-- **检查安排**：留大便检查以明确有无出血；预约后天做胃镜检查，患者要求后天以便爱人陪同，医生同意。
-- **生活方式**：建议戒烟、少喝酒，因吸烟饮酒可能加重胃部疾病；注意避免熬夜，因工作紧张劳累可能诱发疼痛。
-- **复诊与陪同**：胃镜活检后恰逢张大夫查房，便于进一步诊治；患者爱人后天可请假陪同。
+- **检查安排**：留大便检查，以排查出血；胃镜预约在后天进行，患者需确保爱人陪同。
+- **生活方式**：建议戒烟，尽量少喝酒，因吸烟饮酒可能加重胃部疾病；注意休息，避免过度劳累和熬夜。
+- **复诊与沟通**：严医生将总结病情向张医生（上级教授）汇报，再讨论治疗。
 | 药品名称 | 用法用量 | 注意事项 |
 | --- | --- | --- |
-| 奥美拉唑 | — | — |
+| 奥美拉唑 | 每日4-5次（原为每日2次，每次1颗，效果不佳后加量） | — |
 | 阿莫西林 | — | — |
-| 胃炎合剂 | — | — |
+| 胃炎合剂（医务室自配） | — | — |
+# 病情说明与沟通
+- **病情解释**：医生解释婶婶（无血缘关系）的胃癌与患者无直接关联，不必过早担心。
+- **治疗选择**：医生表示等检查资料全面后再判断是否需要手术，若药物能控制病情则无需手术。
+- **患者顾虑**：患者担心是否患胃癌，以及是否需要手术；因工作忙且领导安排出国进修，希望尽早安排。
+- **患者决定**：患者同意留大便检查，并要求胃镜改至后天（因爱人可请假陪同），医生同意。
 # 复诊与预警信号
-复诊时间：后天做胃镜检查，胃镜活检后由张大夫查房。
-⚠️ 需立即就医的预警症状：原文未提及。</t>
+复诊安排：胃镜预约在后天进行，患者需留大便检查；严医生将总结病情向张医生汇报后再讨论治疗。需观察的变化：若出现黑便、呕吐等症状加重，应及时就医。</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>38.1</v>
+        <v>44.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8519/1010</t>
+          <t>8519/1396</t>
         </is>
       </c>
     </row>
@@ -6765,53 +6777,46 @@
       <c r="C18" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审案件，由最高人民法院依法组成合议庭公开开庭审理。庭审围绕三个争议焦点展开：一是抵押权与融资租赁所有权冲突问题，二是罚息、复利计算问题，三是违约金连带责任问题。各方充分发表意见后，合议庭休庭评议并提出调解方案，各方均无异议，同意签署调解协议。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决，向最高人民法院提起上诉。合议庭依法组成并公开开庭审理，围绕抵押权与融资租赁所有权冲突、罚息复利计算、违约金承担三个争议焦点展开法庭调查与辩论。各方充分发表意见后，合议庭休庭评议并提出调解方案，各方均无异议，法院确认调解协议并出具调解书。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国开行） | 请求撤销一审判决相关部分，改判支持其利息、罚息、复利计算主张及违约金请求 | 主张其审查义务仅限于抵押人曲靖电力公司，已尽合理审慎义务；2018年核查时曲靖电力公司名下无融资租赁登记，构成善意取得；罚息、复利计算有合同依据；东源煤电未配合办理账户管理及柜台签约手续，构成违约，应支付千分之一违约金 |
-| 被上诉人（东源电力、东源曲靖电力） | 请求驳回上诉，维持原判 | 主张国开行未在抵押时查询融资租赁登记，不构成善意取得；罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条；国开行宣布贷款提前到期未给合理期限，不符合合同约定；国开行未举证东源煤电违反柜台协议，且未发出限期纠正通知，主张违约金不符合合同约定 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持原判 | 主张国开行未在抵押时查询融资租赁登记，不构成善意取得；其2012年已取得设备所有权，国开行2015年抵押登记在后；东源煤电出资行为系无权处分；融资租赁登记系行业指导性规范，不当然产生物权后果 |
+| 上诉人（国开行） | 请求撤销一审判决，改判支持其利息、罚息、复利计算方式及违约金请求 | 主张其审查义务仅限于抵押人曲靖电力公司，已按央行规定查询融资租赁登记系统，未发现融资租赁记录，抵押登记为法定登记，应构成善意取得；主张罚息自2018年6月13日宣布贷款到期日起算，复利按合同第六条第四款约定计算；主张东源煤电违约应支付千分之一违约金 |
+| 被上诉人（东源电力、东源曲靖电力） | 请求驳回上诉，维持一审判决 | 主张合同约定限期偿还而非立即到期，宣布提前到期应给合理期限；主张罚息不应计收复利，援引最高人民法院2015年、2016年判例；主张国开行未举证证明违约行为，且未按合同约定发出限期纠正通知 |
+| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 主张国开行在2015年办理抵押时未进行有效查询，不构成善意取得；主张东源煤电2012年已取得设备所有权，其出资行为系无权处分；主张融资租赁登记系行业指导性规范，不产生物权效力 |
 # 举证与法庭调查
 ## 举证与质证
-- **国开行提交证据**：2018年9月对曲靖电力公司的融资租赁查询证书，证明其已尽审查义务；招银租赁质证认为该查询证书不符合要求，依据2014年93号文《中国人民银行关于融资租赁登记系统规定》，国开行在抵押时点未进行相应查询。
-- **国开行提交证据**：工商部门出资证明及权属证明（证据四冶合成58亿），证明已对设备所有权尽到合理审慎义务；招银租赁质证认为工商登记公示的是出资行为而非动产所有权，东源煤电出资行为系无权处分。
-- **招银租赁提交证据**：回租设备清单（一审证据7页），载明设备名称、生产厂家，但未载明型号；国开行质证认为该清单无法识别设备唯一性，且铭牌生产日期均在2013年以后，与清单提示的2012年3月1日不符。
-- **招银租赁提交证据**：2013年和2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行质证认为该报告已载明设备出资事项，招银租赁应当知道设备出资情况。
-- **国开行提交证据**：2018年核查表（证据108页），证明曲靖电力公司名下无融资租赁登记；招银租赁质证认为该核查表系诉讼中截图，不能证明抵押时点已查询。
-## 证人/鉴定陈述
-未提及
+- **国开行提交**：2018年9月对曲靖电力公司的融资租赁查询证书，证明其已尽查询义务；招银租赁质证认为该查询证书不符合2014年93号文要求，国开行在抵押时点未进行有效查询。
+- **国开行提交**：2018年6月13日向东源煤电、东源煤业发送的两份催收函，要求归还贷款本金，证明贷款提前到期；东源公司质证认为合同约定限期偿还而非立即到期。
+- **国开行提交**：工商部门出资证明、设备权属证明等材料，证明已对设备所有权尽审慎审查义务；招银租赁质证认为东源煤电出资行为系无权处分。
+- **招银租赁提交**：回租设备清单（证据7页），载明设备名称、生产厂家，但无型号；国开行质证认为无法据此识别设备唯一性。
+- **招银租赁提交**：2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行质证认为该报告已载明设备出资事项。
+- **招银租赁提交**：2018年核查表（证据108页），显示曲靖电力公司名下无融资租赁登记；国开行质证认为该核查表系诉讼中截图，不能证明抵押时点查询情况。
+## 证人、鉴定与其他来源陈述
+- **东源公司代理人陈述**：2015年12月2日发送的邮件及附表，载明招银租赁抵押物为恩洪电厂设备资产，抵押手续正在办理，但未明确区分国开行与招银租赁的设备。
+- **招银租赁代理人陈述**：2012年8月对东源煤电设备进行物权确权审查，要求提供六项设备买卖合同、大部分发票及到货确认单，设备交付即取得所有权。
+- **招银租赁代理人陈述**：初始登记时上传的附件清单包含设备名称、数量、禁止出场时间、生产厂商及存放地点（登封矿区梅干石电厂），该电厂仅有两台汽轮机、两台发电机、两台锅炉。
 ## 法官询问
-- **审判员询问**：中国人民银行征信中心融资租赁登记的性质及法律后果？国开行代理人认为系行业强制规范，招银租赁代理人认为系行业指导性规范，东源公司代理人认为不当然产生物权后果。
-- **审判员询问**：融资租赁登记系统查询方式能否保证查询到登记结果？国开行代理人称只能按单位名称查询；招银租赁代理人称可按公司名称或设备查询，但设备查询涉及种类物区分问题。
-- **审判员询问**：国开行贷款前审查是否有内部规定要求必须查询融资租赁登记，未查到需将查询单作为风控材料？国开行代理人称无此规定，因未查到结果故未保留查询单。
-- **审判员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁代理人称非必填项，本案设备无唯一标识码，故未登记。
-- **审判员询问**：查询通知规定银行办理抵押前应查询，违反该规范是否导致最高人民法院相关司法解释的适用？国开行代理人认为系基本查询义务，已对抵押人完成审慎调查；招银租赁代理人认为银行未查询即违反行业规范，应承担不利后果。
-- **审判员询问**：若通过其他渠道获知设备存在租赁，是否仍需通过央行系统查询？招银租赁代理人认为仍需查询，因央行规定出台背景即实务中大量纠纷，其他方式无法证明善意。
-- **审判员询问**：不同登记机构产生登记瑕疵时，各方有何意见和建议？国开行代理人认为系系统信息不完整、体系相互隔离所致；东源公司代理人称非专业机构，无具体建议；招银租赁代理人建议从立法层面统一规范，发挥行业协会作用，并推动登记平台统一。
+- **审判员询问**：中国人民银行征信中心融资租赁登记的性质及法律后果？国开行代理人认为系行业强制性规范，招银租赁代理人认为系行业指导性规范，不产生物权效力。
+- **审判员询问**：融资租赁登记系统查询方式能否保证查询到登记结果？招银租赁代理人称可通过公司名称或设备信息查询，但设备查询涉及种类物区分问题。
+- **审判员询问**：国开行贷款前审查是否有内部规定要求查询融资租赁登记并保留未查询到结果的单子？国开行代理人称无此规定，因未查询到结果故未保留。
+- **审判员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁代理人称非必填项，本案设备无唯一识别码。
+- **审判员询问**：查询通知规定银行办理抵押前应查询，违反该规范的法律后果？国开行代理人称系基本义务，招银租赁代理人称未查询即违反行业规范。
+- **审判员询问**：不同登记机构产生登记瑕疵的看法？国开行代理人称系统信息不完整是整体问题，招银租赁代理人建议从立法层面统一规范。
 ## 争议焦点与辩论
-### 争议焦点一：抵押权与融资租赁所有权冲突
-- **国开行主张**：其审查义务仅限于抵押人曲靖电力公司，已尽合理审慎义务，2018年核查时曲靖电力公司名下无融资租赁登记，构成善意取得。
-- **招银租赁主张**：国开行未在抵押时查询融资租赁登记，不构成善意取得；其2012年已取得设备所有权，国开行2015年抵押登记在后。
-- **东源公司主张**：其2015年12月2日发送的邮件已用红色标注抵押设备与招银租赁设备名称一致，国开行作为专业金融机构应尽注意义务。
-- **国开行反驳**：邮件系贷后审查材料，非针对抵押物的告知；统计表中招银租赁栏记载的抵押类型为不动产抵押，与融资租赁不同，无法得出已告知的结论。
-### 争议焦点二：罚息、复利计算
-- **国开行主张**：利息计算至2018年6月12日合计2179万5727.08元，罚息自2018年6月13日至2019年2月19日合计4105万零579.57元，复利自2018年3月21日至2019年2月19日合计191.8206万元。
-- **东源公司主张**：罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条；国开行宣布贷款提前到期未给合理期限，不符合合同约定。
-- **国开行反驳**：合同第六条第四款明确约定罚息计收复利，且东源煤电未上诉，一审已支持罚息复利部分。
-### 争议焦点三：违约金连带责任
-- **国开行主张**：依据借款合同第24条第三项，东源煤电应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台签约手续，构成违约。
-- **东源公司主张**：国开行未举证东源煤电违反柜台协议，且未发出限期纠正通知，主张违约金不符合合同约定。
+- **争议焦点一：抵押权与融资租赁所有权冲突**。国开行主张其审查义务仅限于抵押人曲靖电力公司，已按央行规定查询融资租赁登记系统，未发现融资租赁记录，抵押登记为法定登记，应构成善意取得；招银租赁主张国开行在2015年办理抵押时未进行有效查询，不构成善意取得，且东源煤电2012年已取得设备所有权，其出资行为系无权处分。
+- **争议焦点二：罚息、复利计算**。国开行主张利息计算至2017年12月20日，罚息自2018年6月13日起算，复利自2018年3月21日起算，利息合计2179.572708万元，罚息4105.057957万元，复利191.8206万元；东源公司主张合同约定限期偿还而非立即到期，且罚息不应计收复利，并援引最高人民法院2015年、2016年判例。
+- **争议焦点三：违约金承担**。国开行主张依据借款合同第24条第三项，东源煤电违约应支付千分之一违约金，且未按合同第13条、第14条配合办理账户管理及柜台签约手续；东源公司主张国开行未举证证明违约行为，且未按合同约定发出限期纠正通知，违约金请求不符合合同约定。
 # 庭审结果
-本案经合议庭评议，各方当事人对调解方案均无异议，同意签署调解协议。调解方案主要内容：国开行对东源公司债权扣除已清偿本金后，利息、罚息、复利合计6474.4513万元；招银租赁对涉案六项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权，招银租赁对六项设备有所有权；双方同意整体盘活处置设备，变现款各50%，费用各担50%；若变现不足，招银租赁未实现债权按破产重整计划预留方案实现；各方对一审判决第二项、第四项无争议。合议庭将根据《中华人民共和国民事诉讼法》第97条规定出具调解书。</t>
+本案经合议庭评议，各方当事人自愿达成调解协议，法院予以确认并出具调解书。调解方案主要内容：确认国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元；确认招银租赁对涉案六项设备享有所有权，对应债权数额1377.4137万元；确认国开行对93项设备享有抵押权；招银租赁和国开行对案涉全部发电设备整体盘活处置，变现款双方各50%，费用各担50%；若司法变现不能，双方放弃对案涉设备权益，由东源曲靖电力自主生产经营；各方对一审判决第二项、第四项无争议，按判项内容确认。合议庭指出，本案反映动产抵押权与融资租赁物所有权冲突是司法实践中的普遍性难题，根本原因在于国家尚未建立统一的动产登记制度，将向有关部门提出司法建议。</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>66.3</v>
+        <v>71.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30731/2896</t>
+          <t>30731/2705</t>
         </is>
       </c>
     </row>
@@ -6918,40 +6923,39 @@
       <c r="C19" t="inlineStr">
         <is>
           <t># 候选人概况与面试岗位
-本次面试为公务员结构化面试，共20分钟，回答4道题，由面试官主持、计时员计时，考生逐题作答。四道题分别考察综合分析、组织协调、应急处理和公共服务能力，考生均完成作答，面试结束。
+考生为文科生，未提及学历、专业及工作经历。本次面试为公务员结构化面试，时长20分钟，共4道题，由考官（发言人2）主持，计时员（发言人1）提醒时间。考生逐题作答，四题全部完成，未出现超时或未答情况。面试官未作当场点评，仅在第四题作答过程中由计时员提醒“离本场考试结束还有3分钟”，面试结束前考官询问“请问你还有什么需要补充的吗？”，考生回答“没有要补充的了”。
 # 面试问答纪要
 ## 第一题（综合分析能力）
-- 题目：以绳子对骏马、风筝、陀螺的不同作用为引，谈谈对做好公务员工作的启示。
-- 作答要点：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；引用曾子“吾日三省吾身”强调自我反省；单位应形成紧张、活泼、团结的风气，同事间比较能力而非物质；权利和责任需平衡，建立权利清单和责任清单；以陀螺“连轴转”比喻公务员工作，强调责任感和成就感是动力。
+- 题目：以绳子对骏马、风筝、陀螺的三种作用为引，谈对做好公务员工作的启示。
+- 作答要点：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；引用曾子“吾日三省吾身”强调自我反省；认为单位应形成紧张、活泼、团结的风气，同事间比较能力而非物质；提出权利和责任是风筝的“风”和“绳子”，需建立权利清单和责任清单；以“连轴转”形容公职人员工作，强调责任感和成就感是持续动力。
 ## 第二题（组织协调能力）
-- 题目：作为市政府办公室工作人员小王，负责对本市AI相关企业进行调研，了解发展状况和服务需求，为出台扶持政策提供依据，如何完成好任务。
-- 作答要点：前期补课学习AI知识，学习兄弟城市经验，查阅国务院及省厅指导意见；制定方案分客观（企业发展现状）和主观（政府服务需求）两方面；调研涵盖市场状况、服务需求、管理措施三部分；通过企业对接、调查问卷、座谈会等方式实施；提到共享充电宝信任危机，强调AI发展需及时纠偏。
+- 题目：作为市政府办公室工作人员小王，负责调研本市AI相关企业发展状况和服务需求，为出台扶持政策提供依据。
+- 作答要点：前期补课学习AI知识，学习兄弟城市调研经验，查阅国务院及省厅指导意见；制定涵盖客观（企业发展现状）与主观（政府服务需求）两方面的方案；调研分市场状况、服务需求、管理措施三部分；通过企业对接、调查问卷、座谈会等方式实施；服务需求侧重人才引进、政策倾斜、用地审批、人才培养机制；管理措施参考共享充电宝信任危机，强调规范发展。
 ## 第三题（应急处理能力）
-- 题目：作为市级服务标兵小王，现场模拟答复记者关于居民投诉地下排水管道疏通后没过几天又堵上、街道污水严重、质疑标兵名不副实的情况。
-- 作答要点：解释管道为上世纪90年代修建，老城区改造难度大，夏季用水高峰问题集中；承认工作失职，请求媒体给予改进机会；表示已联系维修师傅，并将管道硬件问题汇报上级，计划通过城市综合保障工程改善。
+- 题目：作为市级服务标兵小王，应对记者关于排水管道问题的投诉。
+- 作答要点：承认工作失职，解释管道建于90年代、老城区改造难度大、夏季用水高峰问题集中；承诺立即联系维修师傅现场维修；长期问题已汇报上级，计划通过城市综合保障工程完善硬件；请求媒体解释政府难处、给予改进机会。
 ## 第四题（公共服务能力）
-- 题目：从公共服务角度谈谈处理道路改造和雨污分流工程引发居民不满的社会矛盾思路。
-- 作答要点：分析主要矛盾是时间上的需求不满足，次要矛盾是噪音、出行和舆论问题；提出督促施工方加快进度，使用防噪墙、洒水降尘；开辟出行便道、通过交通广播推荐路线、鼓励公交出行并增加班次；以公告形式在网络公开透明表达政府举措。
+- 题目：从公共服务角度谈道路改造和雨污分流工程引发社会矛盾的思路。
+- 作答要点：分析主要矛盾是时间上的需求不满足，次要矛盾是噪音、灰尘、出行和舆论问题；措施包括督促施工方加快进度、加防噪墙、洒水降尘、建议替代路线、交通广播推荐路线、鼓励公交出行并增加班次；最后以公告形式在网络发布，公开透明表达政府举措。
 # 能力评估
-| 评估维度 | 推荐评级 | 评估依据（具体事例） |
-| --- | --- | --- |
-| 专业/技术能力 | 未评 | 考生在第二题中自述为文科生，对AI存在知识盲区，计划利用课余时间补课学习AI知识，并查阅国务院及省厅指导意见，体现主动学习意识。 |
-| 项目经验 | 未评 | 考生在第二题中提出调研方案分客观和主观两方面，涵盖市场状况、服务需求、管理措施三部分，并通过企业对接、调查问卷、座谈会等方式实施，体现组织协调经验。 |
-| 沟通协作 | 未评 | 考生在第三题中现场模拟答复记者，解释管道问题原因，承认工作失职，并请求媒体给予改进机会，体现沟通与协作意识。 |
-| 岗位匹配度 | 未评 | 考生在第四题中从公共服务角度分析主要矛盾和次要矛盾，提出加快工程进度、减少噪音灰尘、改善出行、加强宣传和沟通等措施，体现公共服务意识。 |
-| 问题解决能力 | 未评 | 考生在第三题中提出已联系维修师傅，并将管道硬件问题汇报上级，计划通过城市综合保障工程改善，体现问题解决思路。 |
-| 思维逻辑性 | 未评 | 考生在第一题中从绳子对骏马、风筝、陀螺的不同作用引申到公务员工作的启示，结构清晰，逻辑连贯。 |
-| 应变能力 | 未评 | 考生在第三题中面对记者投诉，现场模拟答复，解释原因并承认失职，体现应变能力。 |
+| 评估维度 | 评估依据（具体事例） |
+| --- | --- |
+| 综合分析能力 | 考生从绳子对骏马、风筝、陀螺的三种作用展开联想，分别对应鞭策、平衡、动力，并引用曾子“吾日三省吾身”强调自我反省，提出建立权利清单和责任清单，以责任感和成就感作为持续动力。 |
+| 组织协调能力 | 考生作为小王，提出调研步骤：前期补课学习AI知识、学习兄弟城市经验、查阅国务院及省厅指导意见；制定涵盖客观与主观两方面的方案；调研分市场状况、服务需求、管理措施三部分，通过企业对接、调查问卷、座谈会等方式实施。 |
+| 应急处理能力 | 考生模拟答复记者，承认工作失职，解释管道建于90年代、老城区改造难度大、夏季用水高峰问题集中；承诺立即联系维修师傅现场维修，长期问题已汇报上级，计划通过城市综合保障工程完善硬件。 |
+| 公共服务能力 | 考生从主要矛盾和次要矛盾分析道路改造和雨污分流工程引发的问题，提出督促施工方加快进度、加防噪墙、洒水降尘、建议替代路线、交通广播推荐路线、鼓励公交出行并增加班次，最后以公告形式在网络发布。 |
 # 综合素质
-- **突出亮点**：考生在第三题中主动承认工作失职，并请求媒体给予改进机会，体现责任担当；在第二题中提出通过企业对接、调查问卷、座谈会等多种方式收集信息，方法具体可行。</t>
+- **突出亮点**：考生在第二题中主动提出“因为自身是文科生，对人工智能存在知识盲区，会利用课余时间补课”，体现自我提升意识；在第三题中承认“我确实有做的工作失职的地方”，并承诺立即维修，展现担当。
+- **潜在风险点**：考生在第四题中分析“主要矛盾是时间上的需求不满足”，但未提及具体的时间节点或数据支撑；在第三题中解释管道问题时，未提供具体的维修时间承诺。
+- **推进建议**：面试官未提出明确建议，仅按流程询问“请问你还有什么需要补充的吗？”，考生回答“没有要补充的了”。</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>41.7</v>
+        <v>49.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5808/1546</t>
+          <t>5808/1691</t>
         </is>
       </c>
     </row>
@@ -7020,96 +7024,73 @@
       <c r="C20" t="inlineStr">
         <is>
           <t># 参观概况
-本次参观为故宫博物院一日深度游览，由导游全程讲解，围绕中轴线及东西两路展开，覆盖午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、御花园等主要景点，全程穿插历史典故与建筑特色讲解。游览以午门检票入场为起点，导游依次介绍各殿功能与规制，如午门“明三暗五”结构、太和殿大典用途、乾清宫立储诏书秘密、珍宝馆乾隆养老院布局等；同时沿途标注七处免费盖章点及文创购买规则，并推荐三条不同时长的游览路线。整体过程从早间排队错峰开始，至神武门出宫结束，形成一条完整的故宫保姆级游览攻略。
+本次参观为故宫博物院一日深度游览，由主讲人按中轴线及东西延伸路线进行全程讲解，覆盖午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、御花园等主要景点，穿插历史典故与建筑功能说明。讲解以午门“明三暗五”结构及门洞通行规制开篇，依次介绍太和门御门听政、太和殿盛大典礼、保和殿殿试考场、乾清宫立储诏书等核心内容，并延伸至慈禧储秀宫原状陈列、珍宝馆宁寿全宫及九龙壁等专题。全程同时梳理故宫内七处免费盖章点及文创购买规则，并在结尾总结三条适用不同时长与体力的游览路线，整体构成一份涵盖景点、历史、盖章与路线规划的保姆级游览攻略。
 # 核心看点与讲解
-- **午门**：排队检票处，明朝皇帝在此杖打犯错大臣，清朝皇帝在此举行颁朔之礼。门洞呈“明三暗五”结构，正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次；两侧门走皇亲国戚和文武百官。
-- **太和门广场**：眼前有五座金水桥，中间桥供皇帝行走，挨着中间的两座桥供黄金国器行走，文武百官走最边上的桥。
-- **太和门**：明朝皇帝在此御门听政（上朝的地方），门口铜狮子是故宫六对铜狮中最大的一对，脚踩寰宇象征权力，不建议站在狮子底下合影。
-- **太和殿**：即金銮殿，但并非上朝之地，而是举行盛大典礼的地方，如皇帝登基、皇后册封；文武百官在太和殿广场向皇帝喊“吾皇万岁万岁万万岁”，站位遵循“文东武西”——文官站东边，武官站西边。西边弘义阁是皇帝的银库，东边体仁阁是缎库。
+- **午门**：检票入口，明朝皇帝在此杖打犯错大臣，清朝皇帝在此举行颁朔之礼颁发历书。门洞为“明三暗五”结构，中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，旁门走皇亲国戚和文武百官。
+- **太和门广场**：眼前有五座金水桥，中间桥供皇帝行走，挨着中间的两座桥供皇亲国戚行走，文武百官走最边上的桥。
+- **太和门**：明朝皇帝在此御门听政（上朝），门口铜狮子是故宫六对铜狮中最大的一对，脚踩寰宇象征权力，不建议站在狮子底下合影。
+- **太和殿**：即金銮殿，但并非上朝之处，而是举行盛大典礼的地方，如皇帝登基、皇后册封，文武百官在太和殿广场向皇帝喊“吾皇万岁万岁万万岁”，站位遵循“文东武西”。西边弘义阁是皇帝银库，东边体仁阁是缎库。
 - **中和殿**：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再前往太和殿。
-- **保和殿**：从乾隆五十四年开始作为科举考试殿试的考场；东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》并现场盖章，购买后不能去其他店铺盖章，据说汉字馆印章数量最多。
-- **乾清门**：过了此门即后宫区域，皇帝在此上早朝；东边九卿直房是等级高的大臣等待皇帝召见之处，西边是军机处。门口两尊狮子耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
-- **乾清宫**：皇帝平时睡觉的地方，内有27张龙床，据说是为防止刺客找到皇帝位置；牌匾“正大光明”后藏皇帝立储诏书，皇帝写两份诏书，驾崩后取出对比以防被动手脚。门口有铜鹤与铜龟，旁边有社稷江山金殿，是紫禁城里最小的宫殿，提醒皇帝把江山社稷放在第一位。
+- **保和殿**：从乾隆五十四年开始作为科举考试殿试考场。东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》现场盖章，购买后不能去其他店铺盖章，汉字馆印章数量据说是最多的。
+- **乾清门**：过此门即后宫生活区域，皇帝在此上早朝。东边九卿直房是等级高的大臣等待皇帝召见之处，西边是军机处。门口狮子耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
+- **乾清宫**：皇帝平时睡觉的地方，内有27张龙床，据说是为防止刺客找到皇帝位置。“正大光明”牌匾后藏皇帝立储诏书，皇帝写两份诏书，驾崩后对比验证是否被动过手脚。门口有铜鹤与铜龟，旁边有社稷江山金殿，是紫禁城里最小的宫殿，提醒皇帝把江山社稷放在第一位。
 - **交泰殿**：内放25块传国玉玺。
-- **坤宁宫**：皇后住所，明朝所有皇后都住于此；东北角文创店有5枚免费印章。
-- **储秀宫**：慈禧住了20多年的地方，现为慈禧五十大寿时期原状陈列，慈禧儿子在此出生；旁边文创店有3枚免费印章。
-- **翊坤宫与永寿宫**：翊坤宫和永寿宫位于储秀宫以南，永寿宫西边是东西六宫中唯一被称为殿的太极殿。
-- **慈宁宫与寿康宫**：慈宁宫是康熙给奶奶孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住之处。
-- **冰窖书吧**：内有3枚免费印章，印章造型有批折子的感觉。
-- **断虹桥**：网红打卡地，桥上有形态各异的石狮子，最有名的是“武当狮”。
+- **坤宁宫**：皇后住所，明朝所有皇后都住这里。东北角文创店有5枚免费印章。
+- **储秀宫**：慈禧住了20多年的地方，现为慈禧五十大寿时期原状陈列，慈禧喜欢此处因其子在此出生。旁边文创店有3枚免费印章。
+- **翊坤宫、永寿宫、太极殿**：翊坤宫和永寿宫位于储秀宫南边，永寿宫西边是太极殿，为东西六宫中唯一被称为殿的宫殿。
+- **慈宁宫、寿康宫**：慈宁宫是康熙为奶奶孝庄皇太后修建的养老院，旁边寿康宫是甄嬛（剧中人物）居住之处。附近有冰窖书吧，内有3枚免费印章，盖章时有批折子的感觉。
+- **断虹桥**：网红打卡地，桥上有形态各异的石狮子，最有名的是“捂裆狮”。
 - **武英殿**：后改为陶瓷馆，目前关闭状态，只能在门口看看。
 - **文华殿**：位于东边，与西边武英殿对应“文东武西”，参观时未开放，据说现有一个展览。
-- **箭亭**：清朝皇帝及其子孙练习骑马射箭的地方，旁边商店可购买文创雪糕。
+- **箭亭**：清朝皇帝及子孙练习骑马射箭的地方，旁边商店可购买文创雪糕。
 - **钟表馆**：展示那个年代的钟表造型。
-- **珍宝馆**：强烈建议参观，门口有我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据说是当年烧制琉璃砖瓦弄坏后工匠为保命用木头刷白漆以假乱真。珍宝馆并非单独展厅，院子周围屋子都可参观，游客多，尤其看凤冠需挤进去。此处即宁寿全宫，是乾隆给自己修建的养老院，乾隆退休后未放权仍每天上朝办公；皇极殿1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后为乐寿堂，是故宫里唯一能进去参观的皇家寝室，有二龙戏珠设计；再往后是当年慈禧把珍妃丢进去的珍妃井，井口石并非珍妃被丢入之处。珍宝馆出口右手边商店有3枚免费印章。
+- **珍宝馆**：即宁寿全宫，是乾隆给自己修建的养老院，退休后未放权仍每天上朝办公。门口有我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据说是当年烧制琉璃时弄坏一块，工匠为保命用木头刷白漆以假乱真。皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后为乐寿堂，是故宫里唯一能进去参观的皇家寝室，有二龙戏珠设计。再往后是珍妃井，当年慈禧把珍妃丢进去之处，现井口石非珍妃进入的入口。珍宝馆并非单独展厅，院子周围屋子都需参观，游客多，尤其看凤冠处拥挤。出口右手边商店有3枚免费印章。
 - **东筒子夹道**：长长的夹道，拍照非常出片。
-- **延禧宫与景仁宫**：延禧宫为网红打卡地，旁边景仁宫是当年甄嬛被封为熹妃时住的，珍妃也住过。
-- **御花园**：内有钦安殿，供奉真武大帝；紫禁城靠山景山从天上看酷似闭目盘坐的人像，有人说该造型就是钦安殿供奉的真武大帝。
-- **神武门**：故宫紫禁城北门，游览终点；出门左手边有两个盖章点——角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
+- **延禧宫、景仁宫**：延禧宫为网红打卡地，旁边景仁宫是甄嬛被封熹妃时住的宫殿，珍妃也住过。
+- **御花园**：内有钦安殿，供奉真武大帝，紫禁城靠山景山从天上看酷似闭目盘坐的人像，有人说该造型就是真武大帝。
+- **神武门**：故宫北门，出门左手边有两个盖章点，角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
 # 互动与体验
-- **排队检票**：导游建议早点过来排队，排队检票处即午门，可借此观察午门外观。
-- **午门门洞观察**：从正面看午门有三个门洞，进门后可见变成五个门洞，即“明三暗五”结构；导游提示中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名可出一次。
-- **太和门铜狮子合影提醒**：门口铜狮子为故宫六对铜狮中最大的一对，造型威武、脚踩寰宇，导游建议不要站在狮子底下合影，因大爪子正好盖在头顶，单独给狮子拍照即可。
-- **中和殿与保和殿参观**：中和殿为盛大典礼时皇帝的休息室；保和殿自乾隆五十四年起为殿试考场，导游以“弹幕走一波前途无量”互动祝福观众。
-- **汉字馆盖章体验**：保和殿东北角汉字馆有4枚免费印章，可购买《紫禁城100》由工作人员现场盖章；导游形容盖章“真是盖了帽了”，并提及故宫不止一处可买此书，但每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；据说汉字馆印章数量最多，盖完后可选择邮寄到家或自行带走。
-- **乾清宫参观提示**：可往殿内看“正大光明”牌匾，牌匾后藏皇帝立储诏书；门口有铜鹤与铜龟，旁边还有紫禁城里最小的宫殿——社稷江山金殿。
-- **坤宁宫文创店盖章**：坤宁宫东北角文创店有5枚免费印章，导游提醒别错过。
-- **储秀宫参观与盖章**：储秀宫为慈禧居住20多年的地方，现为慈禧五十大寿时期原状陈列；其子在此出生；旁边文创店有3枚免费印章。
-- **慈宁宫与寿康宫打卡**：慈宁宫为康熙给奶奶孝庄皇太后修建的养老院，旁边寿康宫为甄嬛居住地，导游提醒喜欢看《甄嬛传》的游客可到此打卡。
-- **冰窖书吧盖章**：冰窖书吧内有3枚免费印章，导游称印章造型好，盖章时有批折子的感觉；其本人因已买《紫禁城100》，在此购买了冰嬉图。
-- **断虹桥找狮子**：断虹桥上有形态各异的石狮子，最有名的是“捂裆狮”，导游邀请游客找一找它在哪。
-- **武英殿与文华殿现状**：武英殿改为陶瓷馆但目前关闭，只能在门口看看；文华殿导游去时未开，据说现有一个展览，感兴趣可去看。
-- **箭亭文创雪糕**：箭亭为清朝皇帝及子孙练习骑马射箭之处，旁边商店可买到文创雪糕，导游提问雪糕造型是谁，欢迎在评论区分享。
-- **钟表馆参观**：导游带看钟表馆，感叹“不来不知道钟表竟然还有这种造型，真是开了眼了”。
-- **九龙壁找木头龙**：珍宝馆门口为我国现存三座古代九龙壁之一，左边数第三条白色龙下边有一块明显不同的琉璃，实为木头刷白漆，导游讲述工匠烧坏琉璃后以假乱真的典故，并提问“当时皇上究竟有没有发现这个小细节”。
-- **珍宝馆参观体验**：珍宝馆并非单独展厅，院子周围屋子都值得进去看；导游称每样宝贝都能让人说出感叹词，但游客太多，尤其是看凤冠的“没点技术还真挤不进去”。
-- **乐寿堂参观**：乐寿堂为故宫里唯一能进去参观的皇家寝室，可看到二龙戏珠设计，导游提示会联想到恭王府和珅的卧室。
-- **珍妃井说明**：珍妃井为当年慈禧丢珍妃之处，导游澄清井口上方现为井口石，珍妃并非从那个小眼进去的。
-- **珍宝馆出口商店盖章**：珍宝馆出口右手边商店有3枚免费印章，导游提醒收集印章者别漏了。
-- **东筒子夹道拍照**：东筒子夹道拍照非常出片，是很多小姐姐喜欢来的地方。
-- **延禧宫与景仁宫打卡**：延禧宫为网红打卡地，旁边景仁宫为甄嬛被封熹妃时所住，珍妃也住过。
-- **御花园与钦安殿**：御花园内有钦安殿，供奉真武大帝；导游提及紫禁城靠山景山从天上看酷似闭目盘坐人像，有人说造型就是真武大帝。
-- **神武门出口盖章**：神武门出口左手边有两个盖章点，角楼咖啡有2枚免费印章，故宫文创也有2枚免费印章。
-- **三条游览路线选择**：导游总结三条路线供游客按自身情况选择——第一条走完视频内所有景点，适合打算待一整天的游客，建议早起排队、进门往里冲以错开旅游团，导游本人一天走了3万步；第二条沿中轴线看完坤宁宫后去景仁宫、延禧宫，再逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天；第三条沿中轴线看完坤宁宫后去储秀宫，出来去御花园，从神武门出，约2小时，最省力。
-- **盖章点汇总**：导游标注了七个可免费盖章的位置，供有需要的游客截图保存。
+- **排队检票**：主讲人建议早点过来排队，排队检票处即午门，可借此观察午门外观。
+- **午门门洞观察**：从正面看午门有三个门洞，进门后变为五个门洞，即“明三暗五”结构。
+- **铜狮子合影提醒**：太和门门口铜狮子为故宫六对铜狮中最大的一对，造型威武、脚踩寰宇，象征权力；主讲人建议不要站在狮子底下合影，因大爪子正好盖在头顶上，单独给狮子拍照即可。
+- **汉字馆盖章**：保和殿东北角汉字馆有4枚免费印章，可购买《紫禁城100》由工作人员现场盖章；故宫内不止一处可买到《紫禁城100》，每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；据称汉字馆印章数量最多，盖完后可选择邮寄到家或自行携带。
+- **坤宁宫文创店盖章**：坤宁宫东北角文创店有5枚免费印章，主讲人提醒别错过。
+- **储秀宫文创店盖章**：储秀宫边上有文创店，可免费盖章，共3枚免费印章。
+- **冰窖书吧盖章**：冰窖书吧内有3枚免费印章，印章造型好，盖章时有批折子的感觉；主讲人已买了一本《紫禁城100》，在此又买了一个冰溪图。
+- **断虹桥找狮子**：断虹桥上有形态各异的石狮子，其中最有名的是“武当狮”，游客可自行寻找其位置。
+- **箭亭文创雪糕**：箭亭旁商店可买到文创雪糕，主讲人询问雪糕造型人物是谁，邀请观众在评论区分享。
+- **珍宝馆参观体验**：珍宝馆虽名为“馆”但不是单独展厅，院子周围屋子均可进入参观；馆内宝贝令人惊艳，但游客非常多，尤其是看凤冠的区域，没点技术挤不进去。
+- **乐寿堂参观**：乐寿堂是故宫里唯一能进去参观的皇家寝室，可看到二龙仙楼的设计，让人联想到恭王府和珅的卧室。
+- **珍宝馆出口商店盖章**：珍宝馆出口右手边往里走有商店，可免费盖章，共3枚免费印章。
+- **东筒子夹道拍照**：东筒子夹道是很多游客喜欢来拍照的地方，拍照非常出片。
+- **神武门外盖章点**：神武门出门左手边有两个盖章点，角楼咖啡有2枚免费印章，故宫文创内同样有2枚免费印章。
+- **三条游览路线选择**：主讲人总结三条游览路线供游客按自身情况选择——第一条走完视频内所有景点，适合打算待一整天的游客，建议早起排队、进门后沿中轴线往后走以错开旅游团，一天约走3万步，需注意适当休息和补充水分；第二条沿中轴线至坤宁宫后看景仁宫和延禧宫，再逛钟表馆和珍宝馆，出御花园后从神武门出，约半天逛完；第三条沿中轴线至坤宁宫后去储秀宫，再逛御花园，从神武门出，约2小时，最省力。
+- **盖章点汇总提示**：主讲人标注了七个可免费盖章的位置，供喜欢盖章的游客截图保存。
 # 收获与建议
-## 择时与排队
-- **早起错峰**：建议早起排队，一进门就沿中轴线往里冲，可错开大批旅游团人群；等大部队到达时，已在人少时逛完最重要的几个景点。
-- **全天体力预期**：走完所有景点的路线一天约走3万步，游览过程中需适当休息和补充水分。
-## 路线选择
-- **第一条路线（全天）**：走完视频内提到的所有景点，适合打算在故宫待上一整天的游客；进门后沿中轴线往后走，一天约3万步。
-- **第二条路线（半天）**：进门沿中轴线往后走，看完坤宁宫后去景仁宫和延禧宫，接着逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天逛完。
-- **第三条路线（约2小时）**：进门沿中轴线往后走，看完坤宁宫后去储秀宫，出来去御花园，从神武门出；最省力，适合时间有限、不想走太多路的游客。
-## 盖章点汇总
-- **保和殿东北角汉字馆**：4枚免费印章；可购买《紫禁城100》并现场盖章，据称此处印章数量最多。
-- **坤宁宫东北角文创店**：5枚免费印章。
-- **储秀宫文创店**：3枚免费印章。
-- **冰窖书吧**：3枚免费印章，印章造型好，盖章时有批折子的感觉。
-- **珍宝馆出口商店**：3枚免费印章。
-- **神武门出口左手边角楼咖啡**：2枚免费印章。
-- **神武门出口故宫文创**：2枚免费印章。
-- **《紫禁城100》购买规则**：故宫不止一处可买到，但每家店印章不同；购买后不能去其他店铺盖章，需有所取舍；盖完后可选择邮寄到家或自行携带。
-## 注意事项
-- **午门正门通行规则**：中间正门仅供皇帝行走；皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，旁边两门走皇亲国戚和文武百官。
-- **金水桥通行规则**：想体验皇帝待遇走中间桥，皇亲国戚走挨着中间的两座桥，文武百官走最边上的桥。
-- **太和门铜狮子**：不建议站在铜狮子下合影，其大爪子正好盖在头顶，建议单独给狮子拍照。
-- **太和殿非上朝处**：太和殿是举行盛大典礼的地方（皇帝登基、皇后册封），上朝在太和门（明朝御门听政）和乾清门。
-- **珍宝馆参观**：珍宝馆不是单独展厅，院子周围屋子都要进去看；游客多，尤其看凤冠需挤进去。
-- **珍妃井**：井口上方现放的是井口石，珍妃并非从那个小眼进去的。
-- **陶瓷馆状态**：武英殿改为陶瓷馆，目前关闭，只能在门口看看。
-- **文华殿展览**：导游去时未开，据称现有一个展览，感兴趣可前往。
-- **断虹桥打卡**：桥上石狮子形态各异，最有名的是“捂裆狮”，可自行寻找。
-- **文创雪糕**：箭亭旁商店可买到文创雪糕。
-- **东筒子夹道**：拍照非常出片，适合打卡。
-- **御花园对比**：有游客认为御花园比不过和珅家的后花园。</t>
+## 收获与建议
+- **择时与排队**：建议早起排队，一进门就沿中轴线往里走，可错开大批旅游团人群，等大部队到达时已把最重要景点逛完。
+- **路线选择（全天线）**：走完视频内所有景点，适合打算在故宫待上一整天的游客，一天约走3万步。
+- **路线选择（半天线）**：进门沿中轴线至坤宁宫，看景仁宫、延禧宫，逛钟表馆、珍宝馆，出御花园后从神武门出，约半天逛完。
+- **路线选择（省力线）**：进门沿中轴线至坤宁宫，去储秀宫，出御花园后从神武门出，约2小时，最省力，适合时间有限、不想走太多路的游客。
+- **盖章点（汉字馆）**：保和殿东北角，有4枚免费印章，可购买《紫禁城100》现场盖章。
+- **盖章点（坤宁宫文创店）**：坤宁宫东北角，有5枚免费印章。
+- **盖章点（储秀宫文创店）**：储秀宫边上，有3枚免费印章。
+- **盖章点（冰窖书吧）**：有3枚免费印章，印章造型好，盖章时有批折子的感觉。
+- **盖章点（珍宝馆出口商店）**：珍宝馆出口右手边往里走，有3枚免费印章。
+- **盖章点（神武门外）**：出门左手边角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
+- **盖章注意事项**：故宫内不止一处可买到《紫禁城100》，每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；据称汉字馆印章数量最多。
+- **饮食与休息**：游览过程中别忘了适当休息和补充水分。
+- **拍照建议**：太和门门口铜狮子虽造型威武，但站在其下大爪子正好盖在头上，不建议合影，单独给狮子拍照即可。
+- **珍宝馆参观提醒**：珍宝馆并非单独展厅，院子周围屋子都值得进去看；游客多，尤其看凤冠需挤进去。
+- **陶瓷馆状态**：武英殿改成的陶瓷馆目前关闭，只能在门口看看；文华殿主讲人去时未开，据说现有一个展览，感兴趣可前往。</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>44.8</v>
+        <v>42.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4497/4820</t>
+          <t>4497/3769</t>
         </is>
       </c>
     </row>
@@ -7254,63 +7235,68 @@
       <c r="C21" t="inlineStr">
         <is>
           <t># 访谈概况
-本次访谈以实地走访与对话形式展开，围绕农村与城市留守老人养老问题，访问了村政府/民政局干部、农村留守老人、城市社区社工等对象，旨在了解留守老人养老现状、政策困境及社区服务模式。访谈覆盖三大议题：留守老人生活现状与困境、农村养老政策执行情况、城市社区养老模式探索。整体反馈基调为：留守老人群体规模庞大，存在无人照料、就医困难、孤独寂寞等突出问题；农村养老政策保障水平有限、设施运营经费不足；城市社区志愿者制度与养老服务中心有一定成效，但社工行业面临工资低、人员流失、专业欠缺等困境。
+本次访谈由记者以实地走访方式展开，围绕留守老人养老问题，先后深入农村与城市社区，访问了当地老人、村政府和民政局干部、社区养老社工等对象。访谈目的为了解留守老人生活现状、农村养老政策执行情况、城市社区养老经验及社工服务困境，并探讨解决路径。据2021年社区居家养老现状与未来趋势报告数据，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住，独居老人普遍存在无人照料、无人慰藉、就医困难等问题，甚至发生独居老人去世多日才被发现的事件。整体反馈基调以反映现实困境为主，受访老人表达孤独与缺乏陪伴，干部坦承财政困难与设施运营经费不足，社工则指出行业工资低、流动性大、专业性欠缺等困境，同时城市社区也展示了志愿者帮扶、养老服务中心等积极实践。
 # 核心反馈
-## 农村留守老人
-- **独居比例高**：据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边，无奈独居，仅26.8%的老人与子女同住。
-- **无人照料与就医困难**：独居老人不同程度存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自一人在家中发生意外。
-- **孤独寂寞**：黑龙江绥滨一位独居老奶奶因一个人在家太寂寞，报警谎称有人敲门，只为找个人聊聊天。
-- **独居去世多日才被发现**：上海一名67岁独居老人在家中去世，多日后家中溢出刺鼻气味才被邻居发现；杭州一小区一名67岁独居老人同样在去世数天后才被发现。
-- **老龄化趋势加剧**：发言人2从公安了解到的数据，2021年73万多老人中17.8%左右可能独居，以后可能还会增加；1962年到1965年职工档案出生的人特别多，去年开始退休，过了几年老龄化程度会越来越严重。
-- **经济困难**：当地经济不太发达，生病、锻炼等面临经济困难；子女不在身边，一旦生病住院比较麻烦。
-- **娱乐方式少**：老人娱乐方式少，只能坐在一起聊聊天、打打牌。
-- **养老设施运营经费无后续支持**：之前探索过在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但不是一次性投入，地方财政困难，运营经费后续没有支持。
-- **农村养老金偏低**：每个60岁以上农村老年人每月118元，还要提高一点；农村养老金与工人养老金待遇完全一样，但现在的老年人不公平——60年代的人结婚、砍树要交砍伐金，杀猪要交屠宰税。
-## 村政府/民政局干部
-- **五保户供养标准**：三无人员（无收入来源、无法定赡养人和劳动能力）分集中供养和分散供养；集中供养将生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养五保户每月发475元生活费，另有护理补贴。
-- **低保标准分三档**：残疾人一、二级按国家政策纳入最低生活保障，有160、270、380元三个标准，按家庭状况制定，最起码保证最低生活保障。
-- **每月上门走访**：靠村支两委、志愿者尽量敲门串门宣传政策、搞卫生；每月开一次党员组织会，上午开会，下午搞活动或清洁大扫除，到孤寡老人、留守老人家里走一圈。
-- **上门服务不统一**：所有上门服务的都上门、入户签约的只有一个，有的一个都没有。
-- **改善建议**：请专业施工人进行陪伴；倡导在外务工子女多联系；丰富文化生活、增加娱乐方式；希望老年协会专项执行、专门建养老设施，有固定场地，定期有施工人员或宣传板报、健康知识讲座，并给持续运营经费——不只考虑建设，还要考虑后续持续运营。
-## 城市社区社工
-- **志愿者一对一帮扶**：社区给志愿者划分一对一帮扶，志愿者发现老人住在自家楼下，经过家门口上下楼时天天去看；老人身体不好时天天送菜，定期表彰或志愿者积分兑换，年底可到雷锋超市兑换礼品，让志愿者长期坚持。
-- **发掘中年志愿者**：在原有志愿者基础上发掘一批偏中年一点的志愿者；今年做了小手拉大手活动，从儿童青少年入手，拉动家长加入。
-- **送春联活动**：这周四准备开展送春联活动，邀请书法老师写对联，让孩子们上门给老人家送对联。
-- **中秋做月饼与百家宴**：去年中秋节开展做月饼活动，还做过百家宴，让大家感觉社区就是一个大家庭。
-- **2023年目标**：之前每次活动都是社区策划开展，2023年目标是家长自己组织，社区作为协助者。
-- **养老服务中心**：每个社区成立养老服务中心，提供理疗类活动、按摩、老年大学、心理咨询等服务。
-- **心理问题老人案例**：一位老人心理上出现很大问题，与邻里关系处理不和谐、半夜摔门；社区派志愿者上门，但心理问题不是仅上门能解决的，老人出现抗拒，觉得周围人都是陌生的、没有关心他的人，不接受任何人的建议；经社工日复一日关心照料，现在与邻里关系还算好了，能理解一些、接受一些意见，今天还给社工打来电话说寂寞空虚、得不到人关注。
-- **社工工资低、流失严重**：社工行业迅速发展但工资比较低，影响就业率，很多同学做没多久就垮了，不超过一年就转行。
-- **社工专业欠缺**：很多社工并不是学社工专业出来的，可能图周末玩玩，专业上很欠缺。
-- **项目资金不稳定**：服务需要花钱购买，不一定今年服务了明年又能服务，要看领导能否争取到项目；一年服务成效不明显，资金拨不下来项目就结束，但服务成效不一定达到；整个湖南省这么大，一个街道要花十来万块钱，省里还是拨了钱的。
-- **社工专注力分散**：长沙社工机构做的领域比较多，这次做留守儿童、下次做留守老人，专注力不在一个点上。
+## 农村留守老人（受访者5、6、7、9）
+- **子女外出务工，缺乏陪伴**：受访老人反映村里年轻人大多外出打工，老人独自留守，无人照料、无人说话。受访者6提到「现在80%都是都提醒这个在外面做这些事的，年轻人都卖出去了」。
+- **独居寂寞，渴望交流**：受访者7描述子女外出后自己独自生活，日常只能靠养鸡、喂猪等劳作打发时间；受访者6提到村里60多岁老人很多，平时无人可聊。
+- **就医与日常照料困难**：受访者7提到生病时无人照看，只能自己处理；受访者6反映老人独自在家，身体不适时连开门都困难。
+- **经济来源有限**：受访者7提到子女偶尔寄回100元、鸡蛋等物资，但整体收入微薄，生活拮据。
+## 村政府/民政局干部（受访者2、4）
+- **独居老人基数大且持续增长**：受访者2介绍，据公安数据，2021年当地73万多老人中约17.8%为独居，且因1962—1965年职工档案出生人口多、近年陆续退休，老龄化程度还会加剧，估计至少有两三万独居老人。
+- **独居老人三大痛点**：受访者2归纳为「第一就是没有很多的亲人来陪伴他们，第二呢就是经济比较困难……第三个就是娱乐方式少，就坐在一起聊聊天啊，打打牌呀」；生病住院时子女不在身边尤其麻烦。
+- **养老设施运营经费无后续支持**：受访者2指出，此前探索在农村建养老公共设施、提供日托和休闲娱乐平台，但「不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的」。
+- **五保户供养标准**：受访者2介绍，集中供养的五保户将生活护理补贴直接发给敬老院护理人员、生活费直接发给敬老院；分散供养的五保户每月发475元生活费，另有护理补贴。
+- **低保与残疾人保障标准**：受访者4介绍，一级二级残疾人按国家政策纳入最低生活保障，标准分160、270、380元三档，视家庭状况而定，保证最低生活保障；60岁以上农村老年人每月养老金118元，另有食补电补合计约600来块钱。
+- **养老金待遇不公平**：受访者4指出「农村的养老金跟工人的养老金待遇完全一样，但现在的老年人公平」——60年代的人结婚、砍树、杀猪都要交费，如今养老金待遇却与工人不同。
+- **村两委上门服务有限**：受访者4介绍，靠村支两委和志愿者上门串门、宣传政策、搞卫生，每月开一次党员组织会，下午到孤寡老人、留守老人家中走访一圈；但上门服务人员不固定，入户签约覆盖率低。
+- **政策建议**：受访者2提出四点——请专业施工人员陪伴、倡导在外务工子女多联系老人、丰富文化生活增加娱乐方式、希望老年协会专项建设固定养老设施并保障持续运营经费（含建设与后续运营）。
+## 社区社工（受访者8）
+- **志愿者一对一帮扶有效但需激励**：受访者8介绍，社区为志愿者划分一对一帮扶对象，志愿者可顺路天天探望楼下老人、为身体不好的老人送菜；通过定期表彰和志愿者积分兑换（年底可到雷锋超市兑换礼品）维持志愿者积极性。
+- **活动带动代际参与**：受访者8介绍，今年开展「小手拉大手」活动，从儿童青少年入手拉动家长加入志愿者；本周四将开展送春联活动，邀请书法老师写对联、孩子上门送；去年中秋开展做月饼活动，还做过百家宴，营造「社区就是大家庭」的氛围。
+- **2023年目标：家长自组织、社区转协助**：受访者8表示，此前活动均由社区策划开展，2023年目标是家长自己组织活动，社区作为协助者。
+- **养老服务中心已建成**：受访者8介绍，每个社区都成立养老服务中心，提供理疗类活动。
+- **心理问题老人个案**：受访者8介绍曾帮助一位与邻里关系不和谐、半夜摔门的老人，其心理问题严重、抗拒外界关心，「总觉得周围的人都是陌生的，没有关心他的人」；经社工日复一日关心照料，现与邻里关系好转、能接受建议，但仍会打电话说「寂寞空虚，得不到人关注」。
+- **社工工资低、流动性大**：受访者8指出「社工行业还在迅速的发展，但是他的工资都比较低嘛，所以会影响他的一个就业率……基本上很多同学就没做多久，基本上都垮了，可能不超过一年」。
+- **社工驻点难以持续**：受访者8介绍，每个街道和乡镇派两名社工驻点，主要服务老人和小孩，「但是可能说实在话也很难能够走下来」。
+- **项目资金不稳定、服务不连续**：受访者8指出社工服务需花钱购买，项目资金拨不下来就结束，「今年的服务成效并不是那么的明显……资金的问题，他拨不下来了，项目也结束了，但是服务成效不一定就达到了」；湖南省每个街道服务要花十来万块钱，省里虽拨了钱，但很多社工并非社工专业出身，专业能力欠缺。
+## 记者（受访者1、3）
+- **独居老人问题严峻**：据2021年《社区居家养老现状与未来趋势报告》，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住；独居老人普遍存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自在家发生意外。
+- **独居老人去世多日才被发现案例**：受访者3举例，上海一名67岁独居老人在家中去世，多日后家中溢出刺鼻气味才被邻居发现；杭州某小区一名67岁独居老人同样去世数天后才被发现。
+- **独居老人寂寞报警案例**：受访者3介绍，黑龙江绥滨一位独居老奶奶报警称有人敲门，民警上门调查后老奶奶承认是因独自在家太寂寞、想找人聊天才报警。
+- **城市留守老人社交机会更少**：受访者1指出，相比之下城市小区留守老人与外界社交机会更少，更容易产生孤独、抑郁等情绪。
+- **社工制度困境**：受访者1总结，社工大致分社区社工（小区出资、专服务一个小区）和街道社工（政府出资、负责一条街道所有小区）；困境主要在于社会需求量大而供给不足，政府和社区资金有限难以承担长期专业社工服务费用，大量社工迫于生计转行，阻碍行业长期发展。
 # 关键洞察与建议
-## 农村养老困境与政策缺口
-- **数据事实**：据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边，仅有26.8%的老人与子女同住；发言人2引述公安数据称2021年73万多老人中约17.8%可能独居，且因1962–1965年出生人口集中退休，预计老龄化程度会进一步加剧——由此可判断独居老人基数庞大且呈上升趋势，养老服务的需求将持续扩大。
-- **案例事实**：黑龙江绥滨一位独居老奶奶因独自在家太寂寞而报警称有人敲门，民警上门后老人承认只是想找人聊天；上海一名67岁独居老人去世多日后因家中溢出刺鼻气味才被邻居发现；杭州某小区一名67岁独居老人同样在去世数天后才被发现——这些案例直接支持独居老人存在无人照料、孤独无助及意外发生后无人知晓的高风险。
-- **老人自述**：受访老人反映子女外出打工后无人陪伴，日常无人照看，连敲门无人应答的情况也无人察觉；有老人提到村里60多岁老人很多，年轻人大多外出务工——印证留守老人日常照护与情感陪伴的双重缺失。
-- **政策事实**：五保户分散供养每月生活费475元，另有护理补贴；低保标准分160、270、380元三档，按家庭状况制定；农村60岁以上老人养老金每月118元，与工人养老金待遇不同——由此可判断现行农村养老保障水平偏低，仅能维持基本生活，难以覆盖医疗、照护等额外支出。
-- **设施事实**：发言人2提到此前探索过在农村建设养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续没有支持——说明一次性建设投入后缺乏持续运营资金，设施难以长期发挥作用。
-## 受访者提出的建议
-- **发言人2建议**：请专业施工人员进行陪伴；倡导在外务工子女多与老人联系；丰富老人文化生活、增加娱乐方式；希望老年协会专项执行、专门建设养老设施，有固定场地，定期开展板报宣传或健康知识讲座，且不仅要考虑建设还要考虑后续持续运营经费，才能更好发挥作用。
-- **发言人4做法**：靠村支两委和志愿者上门串门、宣传政策、搞卫生，每月开一次党员组织会后下午开展活动，到孤寡老人、留守老人家中走访——表明基层已在现有资源下尽力开展探访，但覆盖面有限。
-## 城市社区模式与社工困境
-- **志愿者机制**：社区建立志愿者制度，一对一帮扶，志愿者发现老人住在楼下便天天上门查看，老人身体不好时帮忙送菜；定期表彰志愿者，年底可在雷锋超市用积分兑换礼品——该机制以就近帮扶降低探访成本，并通过激励维持志愿者积极性。
-- **代际带动**：今年开展"小手拉大手"活动，从儿童青少年入手拉动家长加入志愿者队伍；本周四准备开展送春联活动，邀请书法老师写对联，由孩子上门送给老人；去年中秋节开展做月饼活动，还做过百家宴——通过活动营造社区大家庭氛围，带动更多家庭参与。
-- **2023年目标**：社区目标是让家长自己组织活动，社区作为协助者——从社区主导转向居民自主运营，以减轻社区策划负担并增强可持续性。
-- **养老服务中心**：每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务——城市社区已具备较完整的养老服务设施。
-- **社工分类与困境**：社区社工由小区出资专门服务一个小区，街道社工由政府出资负责一条街道所有小区；每个街道和乡镇派两名社工驻点，主要服务老人和小孩——但社工工资低，影响就业率，很多同学做不超过一年就转行，专业社工人才流失严重。
-- **项目制局限**：社工服务按项目购买，今年做留守儿童、明年可能做留守老人，专注力分散；项目资金拨不下来就结束，但一年服务成效不一定达到——项目制导致服务不连续，难以积累长期成效。
-- **专业欠缺**：很多社工并非社工专业出身，专业能力欠缺——影响服务质量与行业长期发展。
-- **心理个案**：社工姐姐曾帮助一位心理问题老人，老人与邻里关系不和谐、半夜摔门，志愿者上门时老人抗拒，觉得周围人陌生、没有关心自己的人；经日复一日关心照料，老人与邻里关系好转，能接受意见，还主动打电话说寂寞空虚、得不到关注——说明独居老人心理问题需要长期持续介入，单纯上门探访难以解决深层心理需求。</t>
+## 农村养老现状与政策执行
+- **独居比例高**：2021年报告数据显示，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住，由此判断独居是留守老人最主要的居住形态，无人照料、无人慰藉、就医困难是普遍性问题。
+- **极端案例暴露风险**：黑龙江绥滨独居老奶奶因寂寞报警求聊天；上海、杭州各有一名67岁独居老人去世多日才被发现，说明独居老人缺乏日常监护与应急响应机制。
+- **老人自述困境**：多位受访老人反映子女外出打工、无人陪伴，日常无人照看；有老人提到村中60多岁老人仍被请去做工，反映高龄自养现象普遍。
+- **老龄化趋势加剧**：发言人2根据公安数据指出，2021年当地73万多老人中约17.8%为空巢老人，且1962至1965年职工档案出生人口多、去年开始退休，判断未来几年老龄化程度会越来越严重。
+- **经济困难与就医难**：发言人2归纳当地留守老人问题为经济困难、子女不在身边导致生病住院麻烦、娱乐方式少（只能坐在一起聊天打牌），其中经济困难列首位。
+## 农村养老政策与建议
+- **五保户供养标准**：集中供养的五保户由敬老院接收，生活护理补贴直接发给护理人员、生活费直接发给敬老院；分散供养的五保户每月发475元生活费，另有护理补贴。
+- **残疾人低保标准**：一级二级残疾人按国家政策纳入最低生活保障，分160、270、380元三档，按家庭状况确定标准，保证最低生活保障。
+- **养老金水平**：60岁以上农村老年人每月118元养老金，发言人4认为农村生活艰苦，五六百元基本能满足生活但谈不上宽裕，且指出农村养老金与工人养老金待遇完全一样，但老年人公平感不足。
+- **设施运营经费缺口**：此前探索过在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续没有支持，设施难以持续发挥作用。
+- **干部建议**：发言人2提出四点建议——请专业人员陪伴老人、倡导在外务工子女多联系老人、丰富文化生活增加娱乐方式、希望老年协会专项建设养老设施并保障持续运营经费（不仅考虑建设还要考虑后续运营）。
+- **村级走访机制**：发言人4介绍每月开一次党员组织会，上午开会下午开展活动，到孤寡老人、留守老人家中搞卫生、宣传政策、串门走访，由村支两委和志愿者执行。
+## 城市社区养老经验与社工困境
+- **志愿者一对一帮扶**：社区建立志愿者制度，按就近原则划分一对一帮扶，志愿者发现老人住自家楼下便天天探望，身体不好的老人由志愿者送菜上门。
+- **志愿者激励措施**：定期表彰志愿者、实行积分兑换，年底志愿者可到雷锋超市兑换礼品，以此维持志愿者长期坚持。
+- **代际带动参与**：今年开展"小手拉大手"活动，从儿童青少年入手拉动家长加入志愿者队伍；本周四将开展送春联活动，邀请书法老师写对联、由孩子上门送给老人；去年中秋节开展做月饼活动，还办过百家宴，营造社区大家庭氛围。
+- **活动组织转型目标**：此前活动均由社区策划开展，2023年目标是家长自行组织活动、社区转为协助者角色。
+- **养老服务中心**：每个社区成立养老服务中心，提供理疗类活动，另有按摩、老年大学、心理咨询等服务。
+- **社工分类与出资**：社区社工由小区出资、专门服务一个小区；街道社工由政府出资、负责一条街道所有小区；每个街道和乡镇派两名社工驻点，围绕老人和小孩服务。
+- **社工行业困境**：社工工资低影响就业率，很多社工专业同学做不超过一年就离职；社工服务需花钱购买，项目资金不稳定，今年服务明年不一定能继续，要看领导能否争取到项目；湖南省每个街道社工服务要花十来万块钱，省里虽拨了钱但很多社工并非专业出身，专业能力欠缺。
+- **心理问题老人个案**：社工姐姐曾帮助一位与邻里关系不和谐、半夜摔门的老人，老人抗拒上门关心、与外界隔绝，经日复一日关心照料后心理问题逐渐好转，现在能接受意见、与邻里关系改善，说明持续陪伴对独居老人心理支持有效。</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>45.7</v>
+        <v>52.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5309/3910</t>
+          <t>5309/4397</t>
         </is>
       </c>
     </row>
@@ -7917,106 +7903,112 @@
       <c r="C22" t="inlineStr">
         <is>
           <t># 沟通概况
-班主任林瑞在372班家长会上，面向全体家长介绍了班级基本情况、教师团队、班级存在问题及解决思路、后续计划与措施，并给出家庭教育建议。班级共60人，男生25人、女生35人；教师团队多为老教师和优秀教师，班主任林瑞任教地理学科。会议还包含家长代表张宇波分享家庭教育经验、成立家长委员会（至少三人，自愿报名，已有家长自愿参加），以及保险购买、电子学生证办理、资助政策说明等事项。整体基调为加强家校协同，共同促进学生成长。
+班主任林瑞在372班家长会上，面向全体家长介绍了班级基本情况、教师团队、班级存在问题及解决思路、管理计划与措施，并给出家庭教育建议。班级共60人，男生25人、女生35人，整体班风纪律良好，但存在少数学生周末玩手机游戏、自习课效率低、书写欠佳等问题；教师团队以老教师和优秀教师为主，班主任林瑞任教地理学科。会议还涉及成立家长委员会、保险购买、电子学生证办理、资助政策说明等事项，家长代表张宇波（校长代表）分享了家庭教育经验，强调关注孩子身心健康、尊重孩子、多倾听多交流。会议基调为加强家校协同，共同促进学生成长。
 # 沟通内容
 ## 学习表现
-- **亮点**：班级整体时间观念和执行能力较强，班风班貌纪律良好，教室地面干净、卫生状况好。
-- **亮点**：学生遇到问题会积极向老师请教，班主任林瑞表示学生上课时会主动提问。
-- **亮点**：学生关注老师、会主动向老师汇报情况，尊师意识较好。
-- **需关注**：少数学生思考能力较差，尤其在自习课上，老师在场时表现安静，老师不在时纪律混乱。
-- **需关注**：个别学生书写较差，班主任已与相关家长沟通，建议家长为孩子购买字帖练习书写。
-- **需关注**：自习课效率较低，班主任计划加强班委培训，并给予学生10分钟讨论时间，允许不懂的学生离开座位向老师请教。
+- **亮点**：班级整体时间观念和执行能力有所加强，班风班貌纪律良好，教室地面干净整洁，卫生状况好。
+- **亮点**：学生遇到问题会主动向老师请教，班主任林瑞提到上课时会给学生提问机会，学生能积极上来问问题。
+- **亮点**：班级学生整体书写不错，可从学生手册和抽屉里的架构书看出学习情况。
+- **需关注**：个别学生书写不好，班主任已与家长沟通过，建议家长给孩子买字帖练字；有学生写班级计划时把“372班”写成“172班”，字迹潦草影响辨识。
+- **需关注**：自习课效率较低，班主任在场时学生表现安静，不在场时教室乱哄哄；计划加强班委培训，给学生10分钟讨论时间，不懂的可离开座位去问。
+- **需关注**：少数同学思考能力较差，尤其在自习课上表现明显。
+- **需关注**：下次月考在11月初，学生已在学生手册中定下月考目标，建议家长了解孩子的兴趣爱好和目标想法。
 ## 行为表现
-- **亮点**：班级整体班风纪律良好，卫生状况佳。
-- **需关注**：少数学生周末沉迷玩手机游戏，导致返校后精神疲惫、懒散，约有两三个学生存在手机依赖问题。
-- **需关注**：发现少数男生有网瘾，有学生周末向游戏充值，金额达400元。
-- **需关注**：有学生在周六晚上外出过生日，喝酒后回校一身酒气，还抽烟、玩手机。
-- **需关注**：存在早恋现象，班主任建议家长关注孩子的QQ、抖音、快手等社交账号，留意是否有异常动态。
-- **需关注**：有学生带镜子到校，约10人左右，班主任已要求全部收掉。
-- **需关注**：有学生抽屉里发现小说，班主任建议家长管控孩子阅读内容。
+- **亮点**：班级整体纪律良好，班风班貌好。
+- **需关注**：少数同学（约两三个）周末沉迷玩手机游戏，玩累了导致懒散，精神状态不佳。
+- **需关注**：有少数男生有网瘾，星期六晚上往游戏里充值，有学生充了400元；班主任发现有男生晚上看直播、接触不健康内容。
+- **需关注**：有学生带手机到校，班主任要求手机统一上交至手机存放箱，每个箱子贴好学生名字；要求家长处理家中多余手机，不要留多部手机给孩子。
+- **需关注**：班主任建议家长在周一到周五不定时打电话检查孩子手机是否上交——电话能打通说明手机还在孩子手里，打不通或无人接说明已上交。
+- **需关注**：班主任在抽屉里发现学生带镜子，约10人左右，要求全部收掉，请家长也检查孩子书包。
+- **需关注**：有学生看小说，班主任建议家长管控孩子阅读内容，两个店（书店）让孩子看，有目标后再叫出去看。
 ## 社交与心理表现
-- **需关注**：学生处于初中阶段，生理和心理持续变化，是人生中不稳定的时期，需要家长和老师共同引导。
-- **需关注**：班主任提醒家长关注学生心理健康，发现异常应及时进行心理辅导。
-- **需关注**：班主任在班级调查中发现，只有少数学生知道父母的生日，反映出部分学生对家庭关怀意识不足，班主任已就此进行感恩教育。
+- **需关注**：班主任提醒家长关注学生早恋问题，建议家长加孩子QQ、关注其空间朋友圈、抖音、快手等社交账号，留意是否有多个账号、是否屏蔽家长。
+- **需关注**：学生处于初中阶段生理和心理持续变化的时期，是人生中不稳定的时期，需要培养应对风险的能力。
+- **需关注**：班主任强调学生心理健康是重点关注点，家长发现孩子状态不对应及时进行心理辅导。
+- **需关注**：有学生周末外出过生日，喝酒回来一身酒气还抽烟；周六选择住校的学生须遵守住宿纪律要求。
+- **需关注**：班主任提到有学生谎称没钱多次向家里要钱，实际把钱花在别处；提醒家长关注孩子消费情况，建议生活费每天21–24元、每周不超过150元，避免给过多零花钱。
+- **需关注**：班主任在班级调查“知道父母生日”时举手人数很少，提醒家长加强感恩教育，引导孩子用零花钱给父母买小礼物。
 # 家长反馈
-- **家长代表分享**：张宇波（家长代表）分享家庭教育经验，强调关注孩子身体健康和心理健康，教育孩子先做人、避免不良风气，家长要有平常心、尊重孩子、多倾听多交流，并配合学校制度与老师合作。
-- **家委会成立**：班主任提议成立家长委员会，至少需要三人，自愿报名，已有家长自愿参加。
-- **保险购买**：班主任建议家长为孩子购买保险，约310多元，可自行购买，最后会统计购买情况。
-- **电子学生证**：班主任说明电子学生证套餐78元（移动套餐），方便联系，能办的就办。
-- **资助政策**：班主任说明高中补助打在医保卡上、初中打在卡上，提醒家长注意补助使用，避免学生乱花。
-- **费用管理**：班主任强调不在微信群收取任何费用，由学生交给生活委员，提醒家长防范诈骗。
-- **手机管理**：班主任要求家长配合管理手机，统一上交存放，家长可不定时打电话检查，并提醒家长处理多余手机。
-- **安全教育**：班主任提醒家长关注交通安全（未满16周岁骑电动车危险）、防诈骗、防溺水、防校园欺凌。
-- **心理健康**：班主任建议家长关注学生心理健康，发现异常及时进行心理辅导。
-- **家庭教育建议**：班主任建议家长避免过分关注、放任不管、期望过高等误区，创造和睦家庭气氛，多鼓励少批评。
+- **家长代表分享**：张宇波（校长代表、372班语文老师）以家长身份分享家庭教育经验，强调关注孩子身体健康和心理健康，做人教育是必修技能，先做人再成才；家长要有平常心，帮助孩子面对挫折和失败；尊重孩子，给孩子自由空间，不轻易下消极评价；多倾听多交流，给予关爱与理解；配合学校制度，尊重老师。
+  &gt; “要想让孩子离开，就要让他们学会怎么样做人，千万不能让他们带上不良的风气。”
+  &gt; “无论怎样，那你都是爸爸妈妈心里最优秀的儿子，你先批评他，还是不当，这样的话他会更加的深刻。”
+  - 孩子面临的学习压力很大，需要家长帮助重新定位，放下眼前、向往更远风景。
+  - 孩子心理上追求尊重与要求，家长应真正做到陪伴。
+  - 孩子犯错时先安慰再批评，效果更深刻。
+  - 家长应多抽时间了解孩子在校表现，经常给孩子制定容易达到的小目标，激发潜能。
+  - 家长应避免过分关注、放任不管、期望过高等教育误区。
+  - 家长应关注孩子心理健康，发现异常及时进行心理辅导。
+  - 家长应提醒孩子注意交通安全（未满16周岁骑电动车危险）、运动安全、饮食安全、防诈骗、防溺水。
+  - 家长应关注孩子防校园欺凌，遇到问题第一时间联系班主任。
+  - 家长应多鼓励少批评，给孩子适当压力，但期望不能过高或过低。
+  - 家长应给孩子创造和睦、祥和、稳定的家庭气氛，不在家里聚众打麻将、点外卖，不当着孩子面长时间玩手机。
+  - 家长应关注孩子生活费使用情况，建议每天21-24元、每周不超过150元，防止孩子将钱用于非正常消费。
+  - 家长应关注孩子手机使用情况，管理好手机，防止接触不良内容；可不定时打电话检查手机是否上交。
+  - 家长应关注孩子QQ、抖音、快手等社交账号，关注早恋问题。
+  - 家长应关注孩子书包，检查是否携带镜子等与学习无关的物品。
 # 共识与配合事项
 ## 费用与收费
-- [ ] **家长**：确认水费险收费标准为每两周2元/人，若实际用水超出预算再另行说明
-- [ ] **家长**：确认书费预交11000元尚未结算，待最终核算后多退少补
-- [ ] **家长**：未购买书箱的同学，班主任将退还相应费用
-- [ ] **家长**：少数同学存在约100元左右的无效费用（约70元），班主任后续会逐项公布明细
-- [ ] **家长**：班主任不会在微信群内收取任何费用，所有费用由学生直接交给生活委员，请勿相信群内转账要求
-- [ ] **家长**：注意防范冒充班主任头像进行收费的诈骗行为，涉及转账务必电话核实
+- [ ] **家长**：确认水费险收费标准（每两周2元/人，按月收取），卫生不达标或饮水超量时另行补收
+- [ ] **家长**：确认书费预交11000元（已购5本书），待结算后退还未购书箱同学的相应费用
+- [ ] **家长**：关注少数同学约100元、70元、120元、123元等不同额度的费用明细，班主任会逐一公布
+- [ ] **家长**：所有费用由学生交给生活委员，不在微信群内转账缴费
+- [ ] **家长**：警惕冒充班主任头像在群内收费的诈骗行为，一律不信不转
 ## 保险
-- [ ] **家长**：建议为学生购买保险，费用约310多元，可自行选择购买渠道（学校、保险公司、线上平台均可）
-- [ ] **家长**：购买后配合班主任统计是否已购买，确保每名学生都有保障
+- [ ] **家长**：自愿为学生购买保险，费用约310多元，可在学校、菜市场或阿里巴巴等渠道自行购买
+- [ ] **班主任**：统计全班学生保险购买情况，确认是否已参保
 ## 电子学生证
-- [ ] **家长**：电子学生证套餐为78元/月（移动套餐），方便学生请假时联系家长
-- [ ] **家长**：目前班级仅有两个可用坐席，第三个坐席将于9月20几号到期，到期后需办理新号码
-- [ ] **班主任**：将把新号码发到家长群，请家长重新登记补充
-- [ ] **家长**：能办理电子学生证的尽量办理，方便家校联系；无法办理的请说明情况
+- [ ] **家长**：自愿办理电子学生证，移动套餐满78元/月可办理，方便与孩子联系及请假沟通
+- [ ] **家长**：班级现有老年机部分已停机（因诈骗电话多被误判），有可用号码的请及时更新
+- [ ] **班主任**：将新的号码发到家长群，供家长重新登记补充
+- [ ] **班主任**：说明现有坐席到期情况（上届遗留3个坐席，今年9月20几号到期，6月20号已停用）
 ## 资助政策
-- [ ] **家长**：关注家长群内发布的资助政策文件，高中阶段所有补助将打在学生医保卡上（与初中打在卡上不同）
-- [ ] **家长**：每次补助到账后与孩子确认金额及用途，防止学生将补助用于购买手机、过生日、喝酒等非学习消费
-- [ ] **家长**：需要申请补助的学生，学校会协助办理相关手续
+- [ ] **家长**：查阅家长群内已发布的资助政策，注意高中补助与初中不同——所有补助打在医保卡上（非营养餐和生活补助直接上卡）
+- [ ] **家长**：每次补助到账后与孩子确认资金用途（生活费或交回家里），防止用于买手机、过生日、喝酒、抽烟等非正常消费
+- [ ] **班主任**：每次打款后提醒家长核对到账金额
 ## 手机管理
-- [ ] **家长**：配合学校手机管理制度，学生手机统一上交存放，每个手机箱贴好学生姓名
-- [ ] **家长**：家中多余的手机（如家长名下办理的副卡手机）请处理掉或收回，避免学生藏匿使用
-- [ ] **家长**：周一到周五不定时拨打学生电话，若电话能打通但无人接听，说明学生可能未按时上交手机
-- [ ] **家长**：检查学生手机内容，关注是否存在网瘾、观看不健康内容、早恋等情况
-- [ ] **家长**：关注学生QQ、抖音、快手等社交账号，留意是否被屏蔽、是否有多个账号、是否发布不当内容
-- [ ] **家长**：发现学生有网瘾倾向及时干预，避免沉迷游戏
-## 住校纪律
-- [ ] **家长**：提醒住校学生遵守宿舍纪律，周六住校同样须遵守作息要求（2:10回寝室休息）
-- [ ] **家长**：提醒学生不得在宿舍内吸烟、喝酒，外出过生日须提前报备
-## 安全事项
-- [ ] **家长**：提醒学生注意交通安全，未满16周岁不得骑电动车，尤其禁止载人（载2-3人非常危险）；如确需骑行须单人骑行
-- [ ] **家长**：提醒学生注意运动安全、饮食安全
-- [ ] **家长**：提醒学生防范诈骗、防溺水，不得私自下河游泳
-- [ ] **家长**：关注防校园欺凌，学生遇到问题第一时间联系班主任处理
-- [ ] **班主任**：学生遇到矛盾或欺凌事件，第一时间介入处理（举例：曾有一名学生11点反映矛盾，班主任12点即约谈至凌晨2点）
-## 学习与行为管理
-- [ ] **家长**：查看学生手册，书写较差的学生请购买字帖练习（文具店有售）
-- [ ] **班主任**：加强班委培训，提升自习课管理效率；自习课给予学生10分钟讨论时间，不懂的问题可离开座位请教
-- [ ] **班主任**：继续每天加强思想教育工作
-- [ ] **班主任**：制定详细班规，严格请假制度，该扣分扣分、该写检讨写检讨、该罚站罚站
-- [ ] **班主任**：定期与家长沟通学生表现，及时反馈问题
-- [ ] **家长**：关注学生心理健康，发现异常及时进行心理辅导
-- [ ] **家长**：提醒学生合理安排饮食、注意补充营养
-- [ ] **家长**：鼓励学生不懂就问，主动向老师请教问题
-- [ ] **家长**：正确看待成绩，不与其他人盲目比较，帮助学生分析进步与下滑原因
+- [ ] **家长**：配合学校手机管理制度，学生手机统一上交存放（手机箱内每人贴名字）
+- [ ] **家长**：家中多余的手机（含坏手机）及时处理或收走，不留多部手机给孩子
+- [ ] **家长**：周一到周五不定时拨打孩子电话，若打通无人接或关机，说明手机未上交，需及时处理
+- [ ] **家长**：关注孩子手机使用内容，防止接触直播、不健康内容及网瘾问题
+- [ ] **家长**：关注孩子QQ、抖音、快手等社交账号，留意是否被屏蔽、是否有早恋迹象
+## 住校纪律与安全
+- [ ] **家长**：提醒住校学生周六住校期间遵守寝室纪律要求（2:10回寝室休息），不饮酒、不抽烟
+- [ ] **家长**：提醒孩子注意交通安全——未满16周岁不得骑电动车，确需骑行只能一人骑，不得载人
+- [ ] **家长**：提醒孩子注意运动安全、饮食安全、防诈骗、防溺水（不私下结伴游泳）
+- [ ] **家长**：关注防校园欺凌，孩子遇到问题第一时间联系班主任处理
+- [ ] **班主任**：学生生活小事再小也要管好教育好，第一时间处理学生矛盾（如曾深夜12点至2点处理学生纠纷）
+## 班级管理与学习
+- [ ] **班主任**：继续加强思想教育，每天进行
+- [ ] **班主任**：执行详细班规——该扣分扣分、该写检讨写检讨、该罚站罚站，严格请假制度
+- [ ] **班主任**：加强班委培训，提升自习课效率（自习课给10分钟讨论时间，不懂可离座请教）
+- [ ] **班主任**：定期与科任老师沟通，了解学生课堂及各方面表现
+- [ ] **家长**：查看学生手册/记录手册，了解孩子兴趣爱好、月考目标及书写情况
+- [ ] **家长**：书写不好的学生，到文具店购买字帖练习写字
+- [ ] **家长**：关注下次月考时间（11月初），与孩子一起制定合理目标
+## 家长教育配合
 - [ ] **家长**：避免教育误区——不过分关注、不放任不管、不期望过高、不给过多零花钱
-- [ ] **家长**：控制生活费额度，建议每周不超过150元（早餐3-4元、午餐8元、晚餐8元，约21-24元/天）
-- [ ] **家长**：多鼓励少批评，给孩子制定容易达到的小目标，激发潜能
-- [ ] **家长**：创造和睦、祥和、稳定的家庭气氛，不在孩子面前长时间玩手机
-- [ ] **家长**：不在家里聚众打麻将、点外卖，给孩子安静学习环境
-- [ ] **家长**：多抽时间了解孩子在校表现，关注孩子心理动态
+- [ ] **家长**：控制生活费标准——每天21-24元（早餐3-4元、午餐8元、晚餐8元），每周不超过150元
+- [ ] **家长**：关注孩子心理健康，发现异常及时进行心理辅导
+- [ ] **家长**：多鼓励少批评，给孩子适当压力，期望要适当
+- [ ] **家长**：为孩子创造和睦、祥和、稳定的家庭氛围，不在孩子面前长时间玩手机
+- [ ] **家长**：不在家里聚众打牌、点外卖或麻将，避免过多唠叨
+- [ ] **家长**：经常给孩子制定容易达到的小目标（如年级排名120名到30名范围内），激发潜能
+- [ ] **家长**：多抽时间了解孩子在校表现，与孩子多沟通交流
 ## 家委会
-- [ ] **家长**：家委会至少需要3人，自愿报名，已有家长自愿参加
-- [ ] **班主任**：家委会成立后，重要事项经班主任与家长共同探讨决定
-## 其他
-- [ ] **家长**：记住班级号372班、班主任姓名（林瑞），便于家校沟通
-- [ ] **家长**：各科老师电话将发到家长群，有需要可自行联系
-- [ ] **家长**：下午3:20-3:25可前往办理相关业务（保险、电子学生证等），有一节课时间
-- [ ] **家长**：培训期间不得拍照发朋友圈或社交媒体（教官着装不允许拍照），请理解配合</t>
+- [ ] **家长**：自愿报名参加家长委员会，至少需要三人
+- [ ] **班主任**：家委会重大事项经班主任与家长探讨，通过后正式成立
+## 其他事项
+- [ ] **家长**：培训时间3:20开始，下午3点半可办理相关业务（有一节课时间）
+- [ ] **家长**：培训期间禁止拍照，不得发朋友圈或社交媒体（因教官着装不允许拍照）
+- [ ] **家长**：关注校园系统（请假系统）短信通知，了解孩子出入校情况</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>61.1</v>
+        <v>66.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17334/3840</t>
+          <t>17334/4348</t>
         </is>
       </c>
     </row>
@@ -8097,39 +8089,44 @@
       <c r="C23" t="inlineStr">
         <is>
           <t># 例会概况
-10月28日召开自愿级周会，主题为总结工作，会议资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。会上围绕工作方向与任务安排、社区介绍修改、任务分配与执行、待遇与休假等议题展开讨论：工作方向可能偏了、任务工作量需考虑等问题尚待定；社区介绍修改已明确将“我们是谁”提到最前面；任务分配中修订303等已接近完成，下周安排去洛阳；待遇与休假方案已同步。整体态势上，部分任务推进顺利，但工作方向与工作量问题构成当前主要卡点。会议结论为：修改学习介绍、下周安排去洛阳，下一步将邀请同事加入共同制作解决方案。目前有四个任务，包括课程开发、组建执法队伍等，下月主要任务是组建执法队伍，任务具体需招聘20多位师傅。
+本次周会于10月28日召开，会议等级为自愿级，由主持人召集，参会成员以团队角色参与。会议主题为总结工作，资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见、统一对社区的认识。主线议题共六块：会议性质与目标（已定）、工作方向与任务安排（待定，方向可能偏了、需考虑工作量）、社区建设与成员要求（仅同步）、学习介绍修改（已完成）、营销与推广（仅同步）、后续行动（待定）。整体态势上，学习介绍修改顺利收尾，修订303相关文件已差不多完成；但工作方向是否偏了、任务分配具体安排、营销方案及是否继续线下学习均未定，任务工作量可能过大。结论与下一步方向：会议初步统一成员意见，学习介绍已修改完成，下月主要任务为组建执法队伍，下一步开始邀请同事加入并考虑继续线下学习。关键锚点：会议日期10月28日、当前共四个任务、需招聘20多位师傅。
 # 工作进展
-## 工作进展
-- **会议性质与目标**：10月28日召开自愿级周会，主题为总结工作；会议资料包括工作报告、这班看法、这班型社区介绍；目标是初步统一成员意见，统一对社区的认识。
-- **工作方向评估**：提出工作方向可能偏了，需要考虑工作量；需组建教育团队，确定路线并修订纲领章程。
-- **课程开发任务**：目前有四个任务之一，需招聘20多位师傅组建教育班队；第一步确定路线、修订纲领章程，任务开始后安排人员运行。
-- **组建执法队伍**：下月主要任务，为当前最重要任务；需具备政府资源，社区环境建设同步推进。
-- **修订303任务**：已修订了一下，应该已接近完成；需自行查看一遍后打勾确认。
-- **学习介绍修改**：已将“我们是谁”提到最上面；讨论封面和镜头衔接问题，根据修改参数调整。
-- **任务分配**：四个任务直接讲进，需说明为什么做这几件事；任务占比最大的是招聘20多位师傅。
-- **待遇与休假**：上班5000元，额外有奖励和提成；休假为周五半天加周末两天。
-- **下周安排**：安排去洛阳，需排在第二项；下一步邀请同事加入，共同制作解决方案。
-- **账单与发放**：有两个账单未发送，全场活动的优美和棒棒糖待遇尚未发放；发放完才能入职，薪资待遇月会上再发。
-- **仪表盘趋势**：今日余额比上次多，因两个账单未发送导致统计差异。
-- **会议纲要**：讨论是否还需修改，需统一思想讨论。
-- **抖音任务**：需可视化学习方案和工具，根据数据配热情况调整；每月需充值赞助。
-- **企业合规计划**：根据企业实际情况制定企业合规计划。
-- **平台维护**：讨论怎样维护好平台，有线上空间、微信、网站等渠道。
+## 任务与模块
+- **课程开发**：当前四个任务之一，处于任务规划阶段；需结合社区成员按角色（学生、教师、家长、学校、教育主管）划分的需求推进，具体开发内容与进度待进一步明确。
+- **组建执法队伍**：下月主要任务，为当前占比最大的任务；需招聘20多位师傅，组建教育班队，人数尽量控制；任务第一步为确定路线、修订纲领章程，修订303相关文件已差不多完成，待成员自行查看并确认。
+- **学习介绍修改**：✅已完成；已将“我们是谁”提到最上面，并调整两个镜头的衔接；下一步开始邀请同事加入，会后与有意向者沟通。
+- **营销与推广**：🔄进行中；有抖音任务，需可视化学习方案和工具，每月需充值赞助；营销工作了解程度不高，具体方案未确定。
+- **任务分配与优先级**：🔄进行中；当前四个任务需考虑工作量，主持人提出工作方向可能偏了，需统一思想讨论；任务分配的具体安排未明确，需调整优先级（如安排下周洛阳行程的任务排到第二项）。
+## 社区建设与成员管理
+- **社区环境与成员要求**：社区环境很重要，强调“人不出去怎么学习”；按角色分为学生、教师、家长、学校、教育主管，需明确各角色定位与要求。
+- **待遇与休假**：待遇为上班5000元，额外有奖励和提成；休假为周五半天加周末两天。
+- **章程修订**：🔄进行中；修订303相关文件已差不多完成，需成员自行查看并确认；讨论中提及党章修改（坚持四项基本原则改为五个方面），但未形成明确结论。
+# 决定与待办
+- **会议定性与目标**：本次会议定义为周会，日期10月28日，等级为自愿级；会议目标为初步统一成员意见，统一对社区的认识。
+- **学习介绍修改**：学习介绍文件已修改完成，将“我们是谁”提到最上面，并调整两个镜头的衔接。
+- **下月主要任务**：下月主要任务是组建执法队伍；任务一第一步为确定路线、修订纲领章程，修订303相关文件已差不多完成，需招聘20多位师傅。
+- **任务分配调整**：任务分配需考虑工作量，工作方向可能偏了，需要重新评估；四个任务（含课程开发）需按优先级安排。
+- **邀请同事加入**：下一步开始邀请同事加入，会后看有谁愿意参与，共同制作解决方案。
+- **线下学习安排**：考虑继续线下学习，时间已约一小时，可在线下继续。
 # 协作需求
-- **邀请同事加入**：发言人1提出下一步邀请同事加入，共同制作解决方案，会后将看有谁愿意参与；需相关成员配合确认参与意向。
-- **学习介绍修改**：发言人1已完成学习介绍修改（将“我们是谁”提到最上面），下一步需相关成员配合审阅并确认封面与镜头衔接的修改效果。
-- **任务分配与执行**：发言人1提出任务分配需安排，涉及修订303等任务已接近完成，需相关成员配合查看并确认修订结果。
-- **下周去洛阳安排**：发言人1安排下周去洛阳，需相关成员配合确认行程及任务优先级排序。
-- **会议纲要修改**：发言人1询问会议纲要是否还需修改，需相关成员配合反馈意见。
-- **待遇与休假确认**：发言人1提及待遇为上班5000元、额外奖励和提成，休假为周五半天加周末两天，需相关成员配合确认执行细节。</t>
+- **邀请同事加入**：主持人提出下一步开始邀请同事加入，需成员配合参与制作解决方案，会后由主持人联系有意愿者沟通。
+- **任务分配确认**：主持人要求成员查看已修订的303相关文件并自行确认，用打勾方式反馈完成情况。
+- **学习介绍修改**：主持人提出学习介绍中两个镜头衔接需调整，请相关成员按已修改参数进行修改。
+- **营销工作推进**：主持人指出营销工作了解程度不高，需成员共同提高对营销工作的了解，并讨论抖音任务及可视化学习方案和工具的具体方案。
+- **线下学习安排**：主持人提议继续线下共同学习，需成员确认是否参与及时间安排。
+# 待确认与风险
+- **工作方向是否偏了**：主持人提出工作方向可能偏了，需要考虑工作量，但未明确具体偏差与调整方案，待后续确认。
+- **任务分配具体安排未明确**：当前有四个任务（含课程开发、组建执法队伍等），任务分配的具体安排与优先级未在会上敲定，需再议。
+- **营销工作了解程度不高**：主持人表示对营销工作了解程度较高，但未确认其他成员掌握情况，营销具体方案（含抖音任务、可视化学习方案与工具、每月充值赞助）尚未确定。
+- **是否继续线下学习未确定**：会上提出继续线下学习的建议，但未形成结论，待后续决定。</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>26.8</v>
+        <v>33.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4999/1417</t>
+          <t>4999/1898</t>
         </is>
       </c>
     </row>
@@ -8586,38 +8583,42 @@
       <c r="C24" t="inlineStr">
         <is>
           <t># 就诊概况
-48岁男性患者张春和，在成都轻工研究所从事科研工作，于消化内科门诊就诊。主诉上腹烧灼痛4年、近3个月加重，伴两次黑便及近期反酸呕吐。医生初步判断需排查消化道出血及幽门梗阻可能，建议留大便查潜血并预约胃镜。
+48岁男性患者张春和，职业为科研工作（成都轻工研究所），因上腹反复不适4年、近3个月加重就诊于消化内科，为初诊。核心主诉：心窝处烧灼样疼痛，进食冷、硬、刺激性食物或工作紧张劳累时诱发，近3个月白天发作、无夜间痛醒，疼痛可忍受；近4年出现两次黑便（一年前、三个月前各一次），每次持续约一个月，均住院治疗后大便转黄；近两个月出现呕吐，吐出酸水样物，含当日所食食物，偶有隔夜食物。既往16岁患甲肝（已愈），对磺胺药过敏；近期服用斯达舒、奥美拉唑、阿莫西林及胃炎合剂。初步考虑上消化道疾病可能，需进一步检查明确。
 # 病史与背景
-- **现病史**：上腹心窝处烧灼感疼痛4年，每年春季多发，近3个月加重；进食冷、硬、辛辣食物或工作紧张劳累时诱发，白天发作，无夜间痛醒，疼痛可忍受，有完全不痛的时候。
-- **黑便史**：一年前及三个月前各出现一次黑便，每次持续约一个月，均住院数日好转；近3个月大便正常，无黑便。
-- **反酸呕吐**：近2个月出现数次呕吐，呕吐物为酸水，含早晨或中午食物，有时含隔夜食物，呕吐后舒适。
-- **既往史**：16岁患甲肝，在三医院住院一个月，出院及此后体检肝功能均正常；小时候因扁桃体炎在儿童医院就诊。
-- **过敏史**：小时候因扁桃体炎服用磺胺药后左手起红疹，持续半个月，诊断为药物过敏，此后禁用磺胺药。
-- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；婶婶（叔叔的爱人）患胃癌，患者担心自己是否也会得胃癌。
-- **个人史**：吸烟，以前每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝，应酬时少量；每天喝两杯淡茶；双眼近视400度，偶尔口腔溃疡。
-- **近期用药**：近期服用斯达舒，最初一天两次每次一颗有效，后效果不佳，现加至每天四五次仍效果不好；还服用过奥美拉唑（武汉药厂产，国产）和阿莫西林，以及医务室自配的胃炎合剂，服药好转后停药则症状反复。
+- **现病史**：上腹反复不适4年，每年春季多发，近3个月持续；疼痛位于心窝处，烧灼感，进食冷、硬、刺激性食物或工作紧张劳累时诱发，与油腻食物关系不大；近3个月白天发作，无夜间痛醒，疼痛可忍受，工作轻松时有完全不痛的时候。
+- **黑便史**：近4年出现两次黑便，一次在一年前，一次在三个月前，每次持续约一个月，每日最多两次，大便干、形状基本正常；两次均住院治疗，第一次住院约10天，第二次住院两三天，住院后大便转黄。
+- **呕吐**：最近两个月出现几次呕吐，吐出酸水样物，含早晨或中午所食食物，晚上呕吐后舒适，偶有隔夜食物吐出。
+- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；小学时因扁桃体炎在儿童医院服用磺胺药后左手起红疹，持续半个月，医生诊断为药物过敏，此后禁用磺胺药。
+- **个人史**：吸烟，以前每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝；喝淡茶，每天泡两次；工作于成都轻工研究所，从事科研工作，经常加班熬夜。
+- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；婶婶（叔叔的爱人）患胃癌，患者担心自身患病。
+- **近期用药**：近期服用斯达舒（初有效后效果不佳，剂量从每日两次每次一颗增至每日四五次）、奥美拉唑（武汉药厂产）、阿莫西林及医务室自配胃炎合剂，停药后症状反复。
 # 诊断与检查结果
-医生初步判断患者上腹烧灼痛与饮食及劳累相关，结合两次黑便史需排查消化道出血，反酸呕吐物含隔夜食物提示可能存在幽门梗阻。尚未进行胃镜及大便潜血检查，待检查后由上级张医生（指导教授）进一步判断。
+尚未确诊，考虑上消化道疾病可能，需进一步检查明确。患者有两次黑便史，需排查消化道出血；建议留大便检查。预约后天做胃镜，以明确诊断。
 # 治疗方案与医嘱
-- **检查安排**：留大便做潜血检查，以排查出血；预约胃镜，因患者爱人后天可请假陪同，改至后天进行。
-- **生活方式**：建议戒烟、尽量少喝酒，因吸烟饮酒对胃肠道疾病有影响；注意休息，避免熬夜劳累。
-- **复诊与陪同**：胃镜后天进行，由爱人陪同；医生将向上级张医生汇报病情后，再商定下一步处理意见。
+- **检查安排**：留大便检查，排查出血；预约后天做胃镜，因患者爱人可陪同。
+- **生活方式**：建议戒烟、尽量少喝酒，因吸烟饮酒对胃肠道疾病有影响；注意避免熬夜，因工作紧张劳累可诱发症状。
+- **复诊与陪同**：胃镜后由张医生查房；严医生将总结病情向张医生汇报，再商定下一步处理意见。
 | 药品名称 | 用法用量 | 注意事项 |
 | --- | --- | --- |
-| 斯达舒 | 最初一天两次，每次一颗；现加至每天四五次 | 效果逐渐不佳 |
-| 奥美拉唑 | — | 武汉药厂产，国产 |
+| 斯达舒 | 最初每日两次、每次一颗，后增至每日四五次 | 初服有效，后效果不佳 |
+| 奥美拉唑 | — | 武汉药厂产（国产） |
 | 阿莫西林 | — | — |
 | 胃炎合剂 | — | 医务室自配 |
+# 病情说明与沟通
+- **病情解释**：严医生解释婶婶（叔叔的爱人）患胃癌与患者无血缘关系，不必担心遗传风险。
+- **治疗选择**：严医生表示需等检查资料全面后再判断是否需要手术；若能用药物控制病情则无需手术，需手术时再商量。
+- **患者顾虑**：患者担心是否需做手术，因工作繁忙且所里可能安排出国进修，希望如需手术能尽早安排；严医生回应待检查后决定。
+- **患者决定**：患者同意留大便检查，并要求胃镜改至后天以便爱人陪同，严医生同意。
 # 复诊与预警信号
-胃镜预约在后天进行，由爱人陪同。⚠️ 若再次出现黑便或呕吐物带血，需立即就医。</t>
+复诊安排：后天做胃镜，胃镜后由张医生查房；严医生将总结病情向张医生汇报后，再商定下一步处理意见。需观察的变化：若再次出现黑便或呕吐等症状，应及时就医。</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>44.1</v>
+        <v>49.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10297/1139</t>
+          <t>10297/1558</t>
         </is>
       </c>
     </row>
@@ -8956,133 +8957,97 @@
       <c r="C25" t="inlineStr">
         <is>
           <t># 讲座概况
-肖楠总在本次专项讨论会上向投资者汇报过去一年的研究布局、研究成果及投资框架的反思与更新。他首先阐述知识与信息的鸿沟，强调投资者应关注可研究的问题，并介绍市场上两大投资流派（巴菲特代表的务实派与索罗斯代表的务虚派），自认处于中间偏左位置。肖楠明确反对市场上流行的“抱团”和“均值回归”两种观点，认为“抱团”定义不本质，基金经理之间是竞争关系，主观上不可能抱团；均值回归是局部正确，长期看收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。过去一年研究资源投入四个方向：互联网、财富管理行业、新消费和高端制造。投资框架反思共五点：商业模式分类不完备、从商增角度理解商业模式更本质、企业家精神无法定价但长期视角下可能带来超额收益、因终局判断悲观错过中期10倍投资机会、长期变量（如国运、文化背景）可能解释相当部分收益率来源。另有两项补充反思：深度价值可能长期无效（打问号）、小企业X factor驱动企业增长且不被线性描述的因子。客户问答环节，肖楠就终局判断与中期机会、伟大公司判断标准、全市场基金选股逻辑、血制品行业、农林牧渔行业、商增分析、增长曲线、财富管理行业、企业家精神等问题进行回答。
+肖楠总在面向机构投资者的专项讨论会上，以「过去一年的研究布局与投资框架反思」为主题进行汇报并解答客户疑问。肖楠首先强调知识与信息之间存在巨大鸿沟，投资者得到的只是信息而非知识，并介绍市场上以巴菲特为代表的极端务实派和以索罗斯为代表的极端务虚派两大投资流派，自述处于中间偏左位置。肖楠明确反对抱团和均值回归两种流行观点，认为抱团定义不本质，均值回归是局部正确，并举例某商学院老师因相信均值回归在海螺水泥上做波段，两年内错过五六倍涨幅；肖楠指出收益率呈幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。肖楠介绍四大研究布局：互联网、财富管理、新消费和高端制造，并分享对投资框架的五点反思，包括商业模式分类不完备、从商增角度理解商业模式更本质、重视长期变量、对深度价值投资打问号、提出企业X factor概念。本次汇报旨在让投资者了解其研究积累、看问题角度及投资理念框架的更新，对关注基金经理理念升级的基金投资者具有参考意义。
 # 核心观点与论证
 ## 知识与信息的鸿沟
-- **核心观点**：投资者关心的"What happen next"类问题，得到的答案只是信息而非知识，知识与信息之间存在巨大鸿沟。
-- **论据**：肖楠看好某板块或个股，对他而言是基于相关知识（`knowledge`），对投资者而言得到的仅是一条"肖楠看好某某"的信息。
-- **论据**：肖楠今天的观点明天可能因新知识增加而修正，但投资者可能需要等一年甚至更长时间才知道观点已变。
-## 问题分类框架
-- **核心观点**：肖楠将问题分为重要不重要、可研究以及难以研究四类，只关心可研究的问题。
-- **论据**：肖楠关心标的基本面是否发生变化、投资逻辑有没有更新、对标的的认知是否更深入领先。
-- **论据**：作为基金经理，肖楠最关心自己的投资框架有无值得修正和更改的地方，这些是可被研究的。
-- **论据**：该表仅针对肖楠个人，例如基于宏观变量做资产配置的人，美联储利率变化对市场的影响就是既重要又可研究的问题。
+- **核心区分**：肖楠指出，他看好某个板块或个股是基于相关知识（`knowledge`），而听众得到的仅是一条「肖楠看好某某」的信息，知识与信息之间存在巨大鸿沟。
+- **观点易变**：肖楠举例，他今天看好某板块，明天因新知识增加可能修正判断，而投资者可能需要等一年甚至更长时间才知道观点已变，因此「What happen next」类问题的答案对投资者用处不大。
+- **研究问题分类**：肖楠将问题分为重要不重要、可研究以及难以研究四类，他真正关心的是标的基本面是否变化、投资逻辑有无更新、对标的认知是否更深入领先，以及自己的投资框架有无值得修正之处。
 ## 两大投资流派
-- **核心观点**：市场上基金经理的理念和方法大致处于巴菲特代表的极端务实派与索罗斯代表的极端务虚派两个极端之间。
-- **论据**：巴菲特一派认为股票是企业所有权的一部分，价值来源是企业价值即未来现金流，短期波动是随机的、不值得研究，应买入长期持有直到投资逻辑变化。
-- **论据**：索罗斯一派认为股票是筹码，价值来源于其他交易者对筹码的看法，交易代表信息，应研究交易者基于基本面的行为，通过交易与市场对话、试错并获利。
-- **论据**：大部分基金经理包括肖楠处于两个极端中间某一位置，肖楠自认偏巴菲特一侧。
-- **论据**：务实还是务虚没有高下之分，做好的都是大师，做不好都是东施效颦，理念没有好坏。
-## 反对"抱团"说法
-- **核心观点**：肖楠明确反对"抱团"说法，认为该定义不本质，会导致研究误入歧途。
-- **论据**：定义不本质的比喻——若给一叫太阳就出来的动物起名"光明使者"，按此思路理解会误以为宰了它太阳就不出来。
-- **论据**：基金经理之间是竞争关系，主观上不可能抱团，不存在打电话给嘉实基金王经理商量一起买股票的可能。
-- **论据**：同一家基金公司研究员推荐股票获广泛认可、大家买入，若定义为抱团则荒谬，否则需抽取三位幸运基金经理才能买，不可能。
-- **论据**：抱团是截面数据，忽略时间维度；肖楠8年前、5年前买入的标的突然被蜂拥买入，拉长时间看A股和海外股市都有此现象，如当年的五朵金花、眉飞色舞、长牛的医药消费。
-## 反对"均值回归"
-- **核心观点**：肖楠明确反对"均值回归"思想，认为它是特别不本质的局部正确。
-- **论据**：短期看K线图确实均值回归，涨多了跌、死叉金叉，但拉长看无法解释长线牛股10年涨10倍、20倍、50倍、100倍的现象。
-- **论据**：某商学院老师在海螺水泥上做波段，过去10年赚约两三倍，2016或2017年卖出后等回调，两年内股价涨了五六倍，再也没能买回来。
-- **论据**：均值回归90%的时间都正确，但10%的错误代价惨重。
-- **论据**：收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献，挖掉这4%的公司美国股市200年来没有涨。
+- **流派划分**：肖楠认为市场上的基金经理理念和方法大致处于两个极端中间：以巴菲特为代表的「极端务实派」和以索罗斯为代表的「极端务虚派」。
+- **巴菲特派观点**：股票是企业所有权的一部分，价值来源是企业未来现金流，短期波动是随机的、不值得研究，研究重点应放在公司生意和管理层上，买入后长期持有直到投资逻辑变化。
+- **索罗斯派观点**：股票实际上是筹码，价值来源于其他交易者对筹码的看法，交易代表信息、股价波动代表信息，不仅要研究基本面，更要研究交易者基于基本面的行为，通过交易与市场对话、试错并获利。
+- **自身定位**：肖楠自述处于两个极端中间偏左（偏巴菲特）的位置，并强调务实还是务虚没有高下之分，「做好的都是大师，做不好都是东施效颦」。
+## 反对抱团观点
+- **定义不本质**：肖楠认为「抱团」这个定义不本质，会导致研究误入歧途，如同给一叫太阳就出来的动物取名「光明使者」，若据此理解可能误以为宰了动物太阳就不出来。
+- **主观上不可能**：基金经理之间是竞争关系，主观上没有任何抱团意愿，每个基金经理都想买跟别人不一样的东西并获得市场认可，「你去找富国的李经理、嘉实的王经理商量好去抱团」实际不可能。
+- **同公司买入不算抱团**：研究员推荐股票、多位基金经理认可后买入，若定义为抱团则荒谬——「为了防抱团，将来研究员每推荐一个股票就抽取三位幸运基金经理去买」不可能。
+- **忽略时间维度**：抱团是截面数据，忽略了时间维度变化，肖楠举例自己8年前、5年前就买入的标的突然被蜂拥而至的资金追捧，「我们其实也是一脸懵」；A股和海外股市都有此现象，如当年的五朵金花、眉飞色舞、长牛的医药消费等。
+## 反对均值回归
+- **局部正确**：肖楠认为均值回归（跌多了要涨、涨多了要跌）是「特别不本质的局部正确」，短期K线图确实如此，但无法解释10年涨10倍、20倍、50倍、100倍的长线牛股。
+- **商学院老师案例**：某商学院老师在投资理论课上得意地讲，过去10年在海螺水泥上做波段赚了两三倍，每次技术指标都很准；2016或2017年涨一波后卖出等回调，结果两年时间该股涨了五六倍，老师再也没能买回来。
+- **幂律分布**：肖楠强调收益率是幂律分布而非正态分布，做投资的核心是找到摆脱「涨多了又跌、跌多了又涨」规律的特长线超级大牛股；美国股市200年价值增量由4%的公司贡献，把那4%公司挖掉，200年来美国股市没有涨。
 ## 四大研究布局
-- **核心观点**：过去一年研究资源投入四个方向：互联网、财富管理行业、新消费和高端制造。
-- **论据**：互联网——全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业：第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）。
-- **论据**：互联网领域未来仍会出特别大的机会，港股通开通后可投资以前A股未上市的互联网公司。
-- **论据**：财富管理——中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，因巨大基数效应和收入分布密度效应会有巨额剩余财富有待专业机构管理，行业潜在空间远超想象。
-- **论据**：新消费——新一代消费公司从CEO的想法理念到基层执行人员、生产方式、营销方式，与匮乏年代出来的企业完全不一样，不是产品够新而是组织架构和经营理念完全不同。
-- **论据**：高端制造——中国是全球几乎唯一拥有全产业链的国家，微观深入很多制造业细分领域会发现中国已占据主导地位，与10年前"10亿双袜子换台飞机"的理解完全不同；欧美日企业可得的市场份额已是中国企业碗里的肉。
-## 新消费领域研究成果
-- **核心观点**：新消费领域看起来产品差不多的公司，收入利润体量差距巨大，产品差异在三年五年十年维度被放大。
-- **论据**：从外人角度看两家公司卖笔或电饭锅看起来差不多，但深入研究发现产品经理团队或CEO眼中自家产品与竞争对手产品存在巨大鸿沟。
-- **论据**：传统消费领域龙头赚钱、龙二龙三也赚钱，但新消费领域同样巨大的行业里两家公司，一家赚很多钱、另一家完全不挣钱也不知道怎么挣钱。
-- **论据**：从商增角度理解企业商业模式，成长企业商增速度差异巨大，商增过快导致企业走向失败，商增是理解商业模式的重要角度。
-## 投资框架反思一：商业模式分类不完备
-- **核心观点**：过去将生意分为坐地收钱、苦尽甘来、燃烧自己照亮别人三类，但该框架存在不完备性。
-- **论据**：世界上没有一劳永逸的坐地收钱生意，极端稀缺，哪怕爱马仕也会因一个设计师的好坏影响未来五年十年销售。
-- **论据**：长期看所有企业都要死去，不能抱着买千秋万代企业的想法，单一维度出发会错失很多机会。
-## 投资框架反思二：商增角度更本质
-- **核心观点**：从商增角度理解商业模式某种程度上更加本质。
-- **论据**：一些企业从诞生到收入和利润涨100倍，企业结构与诞生之时没有特别大区别，商没有怎么增加就轻易放大100倍。
-- **论据**：另一些企业扩张过程中商增剧烈增加，商增到一定程度后柯斯定理告诉我们企业已没有存在必要。
-- **论据**：过去大量讨论企业在成长过程中靠什么吸收熵增，这是第二点心得。
-## 投资框架反思三：企业家精神定价问题
-- **核心观点**：与张坤争论企业家精神或企业家值不值得定价，无法定价但长期视角下可能带来超额收益。
-- **论据**：企业如日中天时说企业家优秀、估值给50倍，企业犯错误时说企业家不行，导致无法给企业家定价。
-- **论据**：过去特别希望买谁做都一样的生意（如茅台，领导人抓了一批又一批不影响销售），但反过来想，没有这样的公司是否就不投了。
-- **论据**：即使无法给企业家定价，企业发展中一些要素可能在长期视角下带来超额收益，尤其在困难时期，这弥补了三种商业模式分类忽略的因素。
-## 投资框架反思四：终局判断与中期机会
-- **核心观点**：因终局判断悲观错过中期10倍投资机会，应坚持终局判断同时争取研究格局演进的阶段性特征。
-- **论据**：过去投研中因判断企业终局不太好或看不清楚，放弃了一些中期投资机会，甚至错过10倍投资机会。
-- **论据**：具体案例——某企业产品跨代领先竞争对手，当时判断领先不能长期保持、行业格局会变差、ROE剧烈下降，判断正确但企业后来涨了十几倍，过程完全错过。
-- **论据**：可通过紧密跟踪认知快速迭代、识别里程碑式事件来提高胜率，在中期时间内获得好的投资回报率。
-## 投资框架反思五：长期变量
-- **核心观点**：一些特别长期的变量解释了相当一部分收益率来源，需保持谦卑并纳入研究。
-- **论据**：为什么日本、德国、越南没有出巴菲特、索罗斯这样的投资大师，美国有；中国股市20多年诞生一批长线收益好的基金经理，放到台湾、日本、韩国不一定有同样收益率。
-- **论据**：西方世界过去对中国判断中没人预料到中国和平稳定高速发展30多年、40年，这是一个隐藏的巨大变量，称作国运有点不对但也有一点对。
-- **论据**：过去买茅台赚钱的人写的回忆录中列出的逻辑（便宜、产品好、商业模式好）加在一起无法解释茅台过去十年20年如此巨大的涨幅，可能有更大的变量（宏观经济背景、文化背景、品牌背景）在起作用。
-- **论据**：LV、爱马仕等奢侈品牌讲的故事是祖上给皇上当马夫、给娘娘当皮匠，但给的是英国、法国这些老牌资本主义国家的皇上娘娘，因为他们的军舰当年横扫全世界。
-- **论据**：20年前天涯论坛帖子问中国GDP何时超过日本被群嘲，今天大家在算哪一年GDP超过美国。
-- **论据**：30年前洋酒刚进入中国时土豪兑雪碧喝，因为难喝但文化强势、为显示高档；若中国国力强盛到航母在人家十二海里外军事演习，就能讲"纯粮固态发酵的酒才是好酒"的故事。
-- **论据**：未来研究将把特别隐性的长期变量（十年维度起作用）纳入研究。
-## 深度价值可能长期无效
-- **核心观点**：深度价值可能长期无效（打问号，未得结论）。
-- **论据**：深度价值只是一个结果，导致深度价值的原因不变，深度价值最好的结果也就是不输。
-- **论据**：过去投了一些认为是深度价值的标的，结果非常差，产生很大启发和刺激。
-## 小企业X factor
-- **核心观点**：驱动企业增长且不被线性描述的因子（X factor），经典模型无法定价但必须承认存在。
-- **论据**：做DCF、DDM都是线性假设，无非增长率是12、13、14还是15、16、17的区别，但拉长10年视角企业的发展是一条非常漂亮的曲线。
-- **论据**：某理科背景的知名创业家讲企业的发展类似于用直线逼近曲线，短期看线性增长，长期看是曲线。
-- **论据**：经典投资模型中没有变量隐含对企业发展曲率的估计，但现实中大量行业、企业做着同样的事情、生产差不多的产品，差异巨大，原因就是曲率因素在起作用。
-- **论据**：今年遇到的现象——一些企业挺好但估值贵，一些企业便宜但基本面很烂，怎么投是挣扎中的问题。
-- **论据**：今天涨得很大的企业，5年前10年前大家说产品渗透率已很高、利润率已很高，但到今天看当年说的都没实现，企业长出第二、第三生长曲线，这就是有X factor。
-- **论据**：经常强调的超额认知就来自于这些方面。
+- **互联网**：全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国两个国家；中国短短十几年已迭代三代企业——第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）；开通港股通后，以前A股无法投的公司现在可以投，不能容忍在这个领域错失机会。
+- **财富管理**：中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，由于巨大基数效应和收入分布密度效应，会有巨额剩余财富有待专业机构管理，行业潜在空间远超想象。
+- **新消费**：从匮乏年代走出来的第一代、第二代消费品公司与富裕年代诞生的新消费公司完全不同——从CEO的想法理念、基层执行人员、生产方式到营销方式都截然不同，不是产品够新才叫新消费，而是从CEO到组织架构、经营理念完全不一样。
+- **高端制造**：中国是全球几乎唯一拥有全产业链的国家，在很多制造业细分领域已不是被卡脖子，而是「客气一点讲叫占据主导地位」；与10年前「10亿双袜子换台飞机」的理解完全不同，欧美日企业可得的市场份额「已经是中国企业碗里的肉了」。
+## 新消费研究认知
+- **产品差异巨大**：肖楠发现看起来产品差不多的两家公司，收入利润体量差距巨大；深入研究发现，在产品经理团队或CEO眼中，自家产品与竞争对手产品存在巨大鸿沟，这些差异在三年、五年、十年维度里被放得非常大。
+- **行业格局差异**：传统消费领域龙头赚钱、龙二龙三也赚钱是稀松平常的现象；新消费领域同样巨大的行业里可能只有两家公司，一家赚很多钱，另一家完全不挣钱、不知道怎么挣钱。
+## 商业模式反思
+- **三类划分**：肖楠过去把生意分为三类——「坐地收钱」（最喜欢买）、「苦尽甘来」、「燃烧自己照亮别人」（不值得买），至今依然这样划分，但承认框架有不完备性。
+- **没有一劳永逸**：世界上没有一劳永逸的坐地收钱生意，极端稀缺或稀少，哪怕爱马仕这样的企业，一个设计师的好坏也可能影响未来五年十年的销售；长期看所有企业都要死去，单一维度出发会错失很多机会。
+- **商增视角更本质**：有些企业从诞生到收入和利润涨100倍，结构跟诞生之时没有特别大区别，商没有怎么增加就能轻易放大100倍；另一些企业扩张过程中商增剧烈，商增到一定程度后科斯定理就告诉我们企业没有存在必要了；从商增角度理解企业成长过程中的成本项可能更加本质。
+## 企业家精神与长期变量
+- **企业家定价难题**：肖楠常与张坤争论企业家精神或企业家值不值得定价；企业如日中天时企业家估值50倍，开始犯错误就说企业家不太行，导致无法给企业家定价。
+- **长期变量被忽视**：肖楠提出为什么日本、德国、越南没有出巴菲特、索罗斯这样的投资大师，而美国有；中国股市发展20多年诞生了一批长线收益非常好的基金经理，但放到台湾、日本、韩国未必有同样收益率，可能有特别长线的变量解释了相当一部分收益率来源。
+- **国运变量**：西方世界过去对中国判断中，没有人预料到中国和平稳定高速发展30多年、40年，每年都遇到困难但高速发展持续，这是一个隐藏的巨大变量，「你把它称作国运，可能有点不对，但是也有一点对」。
+- **茅台逻辑**：把过去买了茅台赚钱的人写的回忆录中的逻辑全部列出来（便宜、产品好、商业模式好等），加在一起也解释不了过去十年、二十年茅台如此巨大的涨幅，可能有更大的变量（宏观经济背景、文化背景、品牌背景）在后面起作用。
+## 深度价值与X factor
+- **深度价值存疑**：肖楠对深度价值投资打了问号，认为深度价值只是一个结果，导致深度价值的原因不变，那么最好的结果也就是不输；过去投了一些认为是深度价值的标的，结果非常差，产生了很大启发和刺激。
+- **X factor概念**：肖楠提出企业发展的`X factor`——驱动企业增长且不被线性描述的因子；经典投资模型（DCF、DDM）都是线性假设，没有变量隐含对企业发展曲率的估计，但长期起作用的就是这些因素。
+- **增长曲线案例**：某理科班出身的知名创业家告诉肖楠，企业发展类似用直线逼近曲线——短期看每年增长15%、17%是线性的，拉长10年视角是一条非常漂亮的曲线；经典投资模型都不讨论企业发展曲率问题。
+- **无法定价但须承认**：肖楠强调即使无法给X factor有效定价，也一定要承认它的存在，否则会陷入「企业挺好但估值贵、企业便宜但基本面烂」的挣扎；超额认知就来自这些方面。
+## 对终局判断的反思
+- **错过十几倍涨幅**：肖楠反思过去错过一些机会，因判断企业终局不太好或看不清楚而放弃中期投资机会，甚至错过10倍的投资机会；某企业产品跨代领先于竞争对手，当时判断领先不能长期保持、行业格局会变差、ROE会剧烈下降，判断完全正确，但企业足足涨了十几倍，整个过程完全被错过。
+- **调整策略**：肖楠决定在坚持对终局重要性判断的基础上，争取研究格局演进的阶段性特征来把握投资机会；通过紧密跟踪认知快速迭代、识别里程碑式事件来提高胜率，在中期时间内获得好的投资回报率。
 # 金句总结
-&gt; 知识和信息之间是有着巨大的鸿沟的。
-- 讲到投资者关心的"What happen next"问题：主讲人认为听众得到的只是"肖楠看好某某"的信息，而非支撑判断的知识。
-&gt; 务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。
-- 对比巴菲特代表的务实派与索罗斯代表的务虚派时，强调投资理念本身无好坏，执行结果才分高下。
-&gt; 均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。
-- 反对均值回归观点时，以某商学院老师在海螺水泥上做波段、卖出后两年股价涨五六倍再也买不回来的案例佐证。
-&gt; 收益率是幂律分布的，不是正态分布的。
-- 论证均值回归不成立时提出，并引用美国股市200年价值增量由4%公司贡献的数据。
-&gt; 深度价值它只是一个结果，是导致这种深度价值的原因不变，那么深度价值它最好的得到的结果也就是不输了。
-- 反思深度价值投资方式为何长期不成功时提出，并承认自己投深度价值标的结果非常差。
-&gt; 驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。
-- 提出小企业X factor概念时强调，经典投资模型无法定价曲率因素，但长期起作用的正是这些因素。
-&gt; 我们一定要把底线的风险搞好。我们一致同意的就是这个东西它不可被定价。
-- 回答如何把握企业家精神时强调，避免因对企业家认可而犯投资错误，企业家精神不可定价、须谨慎使用。
-&gt; 我们有一些深度的、长期的变量可能是我们所忽略的。
-- 反思长期变量对收益率来源的解释力时提出，并以中国GDP超过日本、白酒出海等话题说明国运等隐性变量的作用。
+&gt; “知识和信息之间是有着巨大的鸿沟的。”
+- 背景：开场论述投资者从基金经理处得到的只是“信息”而非“knowledge”，信息对投资者用处有限。
+&gt; “务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。”
+- 背景：介绍巴菲特务实派与索罗斯务虚派两大投资流派后，说明理念本身无好坏。
+&gt; “均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。”
+- 背景：反对均值回归观点，举例某商学院老师在海螺水泥上做波段，因相信均值回归错过两年五六倍涨幅。
+&gt; “如果你拉长了看，收率是一个极端的极端的幂律分布。”
+- 背景：论证收益率非正态分布，美国股市200年价值增量由4%的公司贡献。
+&gt; “长期看所有的企业都要死去，就是我们不能够抱着……要买一个千秋万代的这种企业。”
+- 背景：反思“坐地收钱”商业模式分类的不完备性，承认没有一劳永逸的生意。
+&gt; “我们尽管穷尽了我们所有的智慧，所有的精力去力求探究我们的这个收益率的来源，往往依然是忽略了一个巨大的变量在后面起作用。”
+- 背景：反思长期变量（如中国和平稳定发展30-40年）对收益率来源的重要影响，主张对市场保持谦卑。
+&gt; “驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。”
+- 背景：提出企业“X factor”概念，经典投资模型无法定价但长期起关键作用。
+&gt; “我们一定要把底线的风险搞好。……这个东西它不可被定价，它不能被定价。”
+- 背景：分享观察企业家精神的心得，强调谨慎归因、不轻易给企业家因素定价。
 # Q&amp;A 环节
-**主持人**：有客户提问，您刚刚讲到在重视终局结果的同时，也更加关注格局演进过程中的阶段性特征和中期投资机会，能否再详细描述一下？
-**肖楠**：这个想法最早来自我们过去错过的一些特别大的机会。我们当时判断某些行业的终局可能不大行，而最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，这类企业有一个重要特征是我们当时忽略的：比如某一代产品当时领先，后来确确实实如我们所料被人追上，但这个企业却做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。所以我们在后来的投资里，开始接受终局可能没有那么强、不会像一劳永逸躺着收钱那么强的判断，在这个前提下依然做出好的投资，希望未来不要再错过类似机会。具体标的我不太好说，但确实有一两个标的给我们带来极大的刺激。
-**主持人**：您在年报中也讲到坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有一些具体的财务指标？
-**肖楠**：伟大公司是在财务指标里面看不出来的。我举一个例子，不能说具体企业：A、B两家公司同属一个大行业但不同细分子行业，投资逻辑很像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高，精细化管理能力和对产品的理解都非常好。但A公司和B公司有一点不一样——B公司不怎么研发，靠管理精益求精做到成本极低，壁垒在于业内络绎不绝来学习但学不会；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人和日本人手里。有意思的是这两家都是国企，A公司在发展初期狠狠被德国人、日本人坑过，从董事长到技术骨干积攒了非常强烈的产业报国、技术报国的理想，从跟着日本人学、跟着德国人学，到越做越强、超越对手、对手跑过来跟他们学，再到做全产业链布局。如果你把这些东西全部写下来，就是一个产业上史诗般壮丽的东西，这种企业就是堪称伟大的企业。
-**主持人**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对于消费以外的行业选股，主要基于什么逻辑？
-**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的不可能三角、企业三阶段、三种商业模式。只不过消费行业基金只许买消费，不能买别的，所以肯定在消费行业里面选。两者的选股逻辑完全一样，没有什么区别。
-**主持人**：您是怎么看待血制品行业的竞争壁垒呢？
-**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开了，因为我们的研究不是特别深入。我们也找了一堆强壁垒的公司，相比之下买了另外的一些。
-**主持人**：在管理行业能否再具体讲一下呢？
-**肖楠**：就血制品这个行业，我们研究的不是特别多。我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有一些特别冲突的观点。
-**主持人**：农林牧渔行业有所提升，请问您对这个行业的观点能讲一下吗？
-**肖楠**：这行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。我们不能在公开场合讲具体股票的投资逻辑。农林牧渔行业的提升不是因为我先看好这个行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。
-**主持人**：您能再具体讲一下生意模式里边商增和商减的分析吗？
-**肖楠**：用直白的理论讲，你们都是企业里的打工人，可以深切感受到：企业从小到大，部门越来越多，以前三五个部门现在十几个，中层干部一大堆，传达效率变低，内部腐败开始出现。企业为了解决这些问题又设巡视检查部门，部门里的人要加工资提级别，这么多部门老总今年提哪个明年提哪个，这些都是商增。企业扩张多一项业务就要多一个副总裁、多很多部门。有些生意收入10个亿和100个亿时没多几个部门，有些企业不需要设那么多高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如有些行业剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生，因为后者从一开始就没考虑好企业大了以后商增怎么处理。而另一家企业基本是高度中央集权，CEO有一个非常强大的情报部门，知道每一件重要事情细入到基层是怎么回事。我特别建议大家去读一读党史，看看这个国家怎么从国民革命时期、抗战时期一直走到现在，组织到今天还能保证这样的活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年这种事在很多国家都会发生。
-**主持人**：您讲到伟大企业的增长曲线，能否对这个曲线的情况再具体讲一下？
-**肖楠**：有些企业你每年看都是线性增长，今年增长20、明年15、后年17.5，但站到10年周期看，跟竞争对手之间拉开了极大差距。举个例子，快递行业，疫情的时候只有顺丰能送，没有疫情时你看不出来，一下子顺丰的业绩和估值把竞争对手甩出一大截。家电领域也是，过去格力一直是老大，美的在做渠道扁平化、T+3，一直没看到成果，突然疫情来了，美的占有率哗一下就上去了，超过了格力。当一些企业在埋头做事、还没体现到报表的时候，我们往往忽略这些事情未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的，平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞。
-**主持人**：由于时间关系，最后两个问题。您刚刚讲到财富管理行业，能否对这个行业具体展开，讲一下投资逻辑和投资机会？
-**肖楠**：财富管理行业这个话题特别大，行业是分层的，顶级富豪、普通中产阶级、中低收入人员的财富管理意味着非常不同的事，有不同的公司和商业模式。我们最早关注这个行业是研究保险的时候，发现某些保险公司一个保险员一单能签七八千的首年保费，有些公司平均一个业务员只有两三千的水平。我们调研了特别厉害的销售和中等销售，发现同样是卖保险，背后的逻辑和机制差异超级大，这些公司的结构设置、激励机制、文化又有巨大差异。去年基金非常火，我们发基金时发现，有些渠道经理过来调研问的问题超级专业，另外一些渠道经理永远问下半年是涨是跌、明年是牛市还是熊市。同样在这个行业混的人，经营结果差距巨大。财富管理行业最大的逻辑在于财富分布超级不均匀，所以有些头部公司真的一口气拿掉行业增量的绝大部分，可能拿掉70%、80%，第二名只能拿到剩下20%的80%。在这种特别偏激、幂律分布的行业里，有可能诞生出特别大的企业。很遗憾，我们有一些产品因为监管和法律规则的原因反而不能投类似标的，但未来合同设置更清晰的时候，我们可能会在这方面的投资上有所体现。
-**主持人**：您讲到第二第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
-**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营成功就说这个企业家特别厉害，就像不要因为一个基金经理业绩好就说他特别厉害。一定要把所有能归因到数据里客观指标的因素全部归因完，再特别谨慎地评价一些比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为这个企业家在，所以公司就能值多少。我强调的一直是避免错误归因，避免因为对企业家认可去犯投资错误，一定要把底线风险搞好。我们一致同意这个东西不可被定价。这些比较虚的因素——技术进步、企业家精神——什么时候考虑？在所有客观归因尽量穷尽以后，可能某种程度上一些收益率的归因要归到这里面去。另外，我们只能在有限范围内做两两比较，比如两家公司做同样生意、同样产品，在这种限定条件下比较两个企业家的水平高低、理念先后，去找你认可的那一家，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，一定要谨慎使用所谓企业家精神、伟大企业这些词，在一些特别极端的时候它可能是你某些信仰上的支持，但尽量不要去用。</t>
+**听众**：您刚刚讲到在重视终局结果的过程中，也更加关注格局演进的阶段性特征和中期投资机会，能否再详细描述一下？
+**肖楠**：这个想法最早来自我们过去错过的一些特别大的机会，非常懊恼。我们之所以错过，是因为判断这些行业的终局可能不大行，而最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，当时完全可以在考虑终局可能没那么好的前提下，依然做出漂亮投资。这类企业有个重要特征是我们当时忽略的：比如某一代产品当时领先，后来确实如我们所料被人追上，但企业深深做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。这让我们很惊讶，刺激很大。所以后来我们渐渐开始接受：即使承认终局没那么强、没那么好，不像一劳永逸躺着收钱那么强，依然能做出好的投资。具体标的不太方便讲，但确实有一两个标的给我们带来极大刺激。
+**听众**：您在年报中也讲到坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有具体的财务指标？
+**肖楠**：伟大公司在财务指标里是看不出来的。我举个例子，不能说具体企业：有两家公司都很厉害，同属一个大行业但不同细分子行业，投资逻辑很像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高。但A公司和B公司有一点不一样——B公司不怎么研发，靠管理上精益求精做到成本低，壁垒也很高；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人、日本人手里。有意思的是这两家都是国企，A公司在发展初期被德国人、日本人狠狠坑过，从董事长到总经理到技术骨干都积攒了非常强烈的产业报国、技术报国的理想。他们从跟着日本人、德国人一步步学，到越做越强超越对手，到对手跑过来跟他们学，到开始做全产业链布局——把这些写下来就是一个产业史诗。这种企业堪称伟大。过去在这个领域，很多位置是日本人、美国人、台湾省的企业家占据的，你会看到中国人在一点点往前拱，这些人不是想今年赚三亿五亿，而是一门心思往前做。如果有机会，未来可能把这些企业的经历写出来。
+**听众**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对于消费以外的行业选股，主要基于什么逻辑？
+**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的不可能三角、企业三阶段、三种商业模式这些。只不过消费行业基金只许买消费，不能买别的，所以肯定在消费行业里选。两者的选股逻辑完全一样，没有什么区别。
+**听众**：您怎么看待血制品行业的竞争壁垒？
+**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开了，因为我们的研究不是特别深入。我们也找了一堆强壁垒的公司，相比之下买了另外一些。
+**听众**：在管理行业能否再具体讲一下？
+**肖楠**：血制品这个行业我们研究得不是特别多。我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有一些特别冲突的观点。
+**听众**：农林牧渔行业有所提升，请问您对这个行业的观点？
+**肖楠**：这个行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。我们不能在公开场合讲具体股票的投资逻辑。不是我先看好农林牧渔行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。
+**听众**：您能否再具体讲一下生意模式里商增和商减的分析？
+**肖楠**：用直白的话讲，你们都在不同机构、企业里，都是打工人，可以深切感受到：企业从小到大，部门越来越多，以前三五个部门，现在十几个，中层干部一大堆，上面分领导、副总裁，下面一大堆基层部门，传达效率变低，内部腐败开始出现。企业为了解决这些问题，要设置部门去巡视检查，又多了一个部门；部门里的人干三五年要加工资、提级别，这么多部门老总今年提哪个、明年提哪个。企业发展到一定程度要多做业务，往下游做或往上游做，多一项业务就要多一个副总裁，又有很多部门。有些生意收入10亿和100亿时没多几个部门，有些企业不需要设那么多副总裁和高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如有些行业就剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生——后者从一开始就没考虑好企业大了以后商增怎么处理。而另一家基本是高度中央集权，CEO有非常强大的情报部门，知道每件重要事情细入基层是怎么回事。我特别建议大家去读党史，看看这个组织怎么从国民革命时期、抗战时期一直走到现在还能保持活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年，在很多国家都会发生。
+**听众**：您讲到伟大企业的增长曲线，能否再具体讲一下？
+**肖楠**：比如你过去几年每年看，这个企业今年增长20%、明年15%、后年17.5%，都是线性的，有些年份差一点增长3%、5%。突然有一天你站到10年周期看，这个企业和竞争对手之间拉开了极大差距。举个例子，快递行业，疫情的时候只有顺丰能送，没疫情时看不出来，一下子顺丰的估值和业绩把竞争对手甩出一大截。如果做线性外推，无非是今年增速快一点、你15别人13，但拉长看，它就是在一些关键点上突然甩出来。家电领域也是，过去格力一直是老大，美的在做渠道扁平化、T+3这些，一直没看到成果，突然疫情来了，美的占有率哗一下就上去了，超过格力。当一些企业在埋头做事还没体现到报表时，我们往往忽略这些事情未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的——平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞。
+**听众**：您刚刚讲到财富管理行业，能否具体展开讲一下投资逻辑和投资机会？
+**肖楠**：财富管理行业这个话题特别大，而且是分层的，顶级富豪、普通中产阶级、中低收入人员的财富管理怎么做，都有不同的公司和商业模式，说起来超级复杂。我们最早是研究保险时发现一些有意思的事：某些保险公司一个保险员一单能签七八千的首年保费，有些公司平均一个业务员只有两三千的水平。我们花了很多时间调研特别厉害的销售和中等销售人员，发现同样是卖保险，背后的逻辑和机制差异超级大，而这些差异来自公司的结构设置、机构设置、激励机制、文化等。去年基金很火，我们发基金时发现，有些渠道经理过来调研问的问题超级专业，另外一些渠道经理永远问下半年是涨是跌、明年是牛市还是熊市。同样在这个行业混的人，经营结果差距巨大，背后的模式也超级不一样。财富管理行业最大的逻辑在于财富分布超级不均匀，会导致有些头部公司一口气拿掉行业增量的绝大部分，比如拿掉70%、80%，剩下的第二名只能拿到剩余20%的80%。在这种特别偏激、幂律分布的行业里，有可能诞生特别大的企业。很遗憾，我们有些产品因为监管和法律规则的原因反而不能投类似标的，但未来合同设置更清晰时，我们可能会在这方面有所体现。
+**听众**：您讲到第二、第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
+**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营成功就说这个企业家特别厉害，就像不要因为一个基金经理过去业绩好就说他特别厉害。一定要把所有能归因到数据里客观指标的因素全部归因完，再特别谨慎地评价一些比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为这个企业家在，所以这个公司就能值多少。我强调的不是怎么通过企业家精神去获得机会，而是避免错误归因，避免因为对企业家认可而犯投资错误。我们一致同意这个东西不可被定价。这些比较虚的因素——技术进步、企业家精神、X factor——什么时候考虑？是在所有客观归因都尽量穷尽以后，再说可能某种程度上一些收益率归因到这里面。另外，只能在有限范围内做两两比较：两个公司做同样生意、同样产品，在这种限定条件下比较两个企业家的水平高低、理念先后，找你认可的那一家，仅此而已，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，要谨慎使用所谓企业家精神、伟大企业这些词，在一些特别极端的时候它可能是信仰上的支持，但尽量不要去用。</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>95.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26252/8715</t>
+          <t>26252/7971</t>
         </is>
       </c>
     </row>
@@ -9247,40 +9212,56 @@
       <c r="C26" t="inlineStr">
         <is>
           <t># 辩论内容概述
-本次辩论赛围绕“拥有让人爱上自己的超能力是否美好”展开，正方为RUC棒辩论队，反方为对方辩友。正方主张爱是自由意志的产物，超能力通过洗脑剥夺对方选择，类似占有而非爱；反方则认为爱非意志可控，超能力是改变自己或创造条件，且掌握在爱你的人手中优于未知命运。双方就超能力是否剥夺自由意志、是否等同于洗脑、真爱本质等核心议题展开交锋，正方在质询与自由辩论中逐步占据优势，最终评委判定正方获胜，获得4分钟小结时间。
+本次辩论赛围绕“拥有让人爱上自己的超能力是否美好”展开，正方为RUC棒辩论队，反方为对方辩友。正方认为超能力本质是洗脑，剥夺对方自由意志，类比强奸违背意志，因此不美好；反方认为爱并非自由意志的产物，超能力机制未知，可能改变自己而非洗脑，因此美好。辩论整体走向围绕超能力是否剥夺自由意志、是否等同于洗脑、真爱本质等核心议题展开交锋，正方在质询环节获胜，获得4分钟小结时间。
 # 核心论点
-辩题为“拥有让人爱上自己的超能力是否美好”，正方主张超能力剥夺自由意志、非真爱，反方主张爱非意志可控、超能力可改变自己或创造条件。双方论点详见下表。
+辩题为“拥有让人爱上自己的超能力是否美好”，正方为RUC棒辩论队，反方为对方辩友。双方围绕超能力的性质、自由意志与真爱的关系展开交锋。
 | 阵营 | 立论框架 | 核心论点 | 支撑论据 |
 | --- | --- | --- | --- |
-| 正方 | 爱是自由意志的产物，超能力剥夺对方选择 | 超能力通过洗脑获取的爱是占有而非爱 | 类比强奸，违背对方意志强行介入亲密关系；真爱应保留对方说“不”的权利；超能力使爱来得太容易可能导致不珍惜 |
-| 反方 | 爱非意志可控，超能力可改变自己或创造条件 | 超能力可改变自己或创造100%符合对方需求的条件 | 爱是玄学，科学无法解释为何偏偏对某人产生爱；将红线交给爱你的人比交给未知命运更可靠 |
+| 正方 | 超能力是洗脑，剥夺自由意志 | 超能力本质是洗脑，剥夺对方自由意志，类比强奸违背意志 | 超能力通过洗脑获取爱，是占有而非爱；洗脑无法换回真爱；爱是自由意志的产物，坠入爱河非跳入爱河 |
+| 反方 | 爱非自由意志产物，超能力机制未知 | 爱非自由意志产物，超能力机制未知，可能改变自己而非洗脑 | 爱是玄学，科学无法解释；超能力可能改变自己或对方；珍惜取决于认真程度，超能力体现真爱 |
+| 正方 | 超能力使爱变质，存在伦理风险 | 超能力使爱变质，因得来太易；可能用于控制、欺骗，类比PUA | 珍惜与难易程度无关；超能力可能用于控制、欺骗；放手的爱才是真爱，应保留对方选择空间 |
+| 反方 | 超能力可拯救爱人，比月老可靠 | 超能力可拯救爱人，比月老可靠；可避免遗憾 | 月老和丘比特不靠谱；超能力掌握在爱你的人手里比交给命运可靠；超能力可避免遗憾 |
+# 争议焦点
+- **焦点**：超能力是否剥夺自由意志；正方：超能力是洗脑，剥夺对方自由意志，类比强奸违背意志；反方：爱非自由意志产物，超能力机制未知，可能改变自己而非洗脑。
+- **焦点**：超能力是否等同于洗脑；正方：超能力通过洗脑获取爱，是占有而非爱；反方：超能力机制未知，不一定是洗脑，可能改变自己或对方。
+- **焦点**：超能力是否使爱变质；正方：超能力使爱得来太易，容易变质；反方：珍惜取决于认真程度，超能力体现真爱。
+- **焦点**：超能力的伦理风险；正方：超能力可能用于控制、欺骗，类比PUA；反方：超能力可拯救爱人，比月老可靠。
+- **焦点**：放手的爱是否必要；正方：爱应保留对方选择空间，放手的爱才是真爱；反方：超能力可避免遗憾，掌握在自己手里比交给命运可靠。
 # 环节交锋
 ## 开篇立论
-- **正方**：爱是自由意志的产物，超能力抹杀了对方的决定；月老和丘比特让有情人终成眷属，若强行牵线则非浪漫。
-- **反方**：爱是玄学，科学无法解释为何偏偏对某人产生爱；超能力可改变自己或创造100%符合对方需求的条件。
-## 质询
-- **正方**：超能力通过洗脑获取的爱是占有而非爱，类比强奸，违背对方意志强行介入亲密关系。
-- **反方**：爱非意志可控，超能力可改变自己或创造100%符合对方需求的条件，且掌握在爱你的人手中优于未知命运。
+- 正方提出超能力是洗脑，剥夺对方自由意志，类比强奸违背意志。反方回应爱非自由意志产物，超能力机制未知，可能改变自己而非洗脑。
+  &gt; “你方认为我们的超能力一定是通过给对面精神洗脑，强行剥夺他自由意志的方式来达成我方不可告人的目的。”
+- 正方以“坠入爱河”非“跳入爱河”反驳反方“爱非自由意志产物”的观点。反方未直接回应。
+  &gt; “什么叫做情非得已，什么叫做情感意境，为什么我们在描述恋爱的感觉的时候，我们说的是坠入爱河，而不是说去跳入爱河。”
+## 质询环节
+- 正方质询反方：超能力是否剥夺对方自由选择，类比强奸违背意志。反方回应：发生性关系由对方决定，但爱上你与自由意志无关。
+  &gt; “强奸这件事情叫做违背妇女意志，强行发生性关系，而今天在面对情况当中，为什么是违背对方意志，强行介入亲密关系。”
+- 反方质询正方：超能力机制未知，可能改变自己而非洗脑。正方回应：洗脑不是爱，且洗脑无法换回真爱。
+  &gt; “洗脑错误，真的能够换回真爱，这个辩题在老师，用这个错误能力可能让你爱的人也。”
+- 正方质询反方：超能力使爱变质，因得来太易。反方回应：珍惜取决于认真程度，超能力体现真爱。
+  &gt; “难道我们在恋爱过程当中珍不珍惜对方这件事情完全看我们之间的新鲜感？”
+- 反方质询正方：超能力可拯救爱人，比月老可靠。正方回应：伤不伤害由你定义，这本身就是自私的来源。
+  &gt; “这些伤不伤害都是你定义的，你自己觉得自己跟他在一起不是伤害，别人跟他在一起是伤害，这其实就是今天讲的自私的来源。”
 ## 自由辩论
-- **正方**：超能力使爱来得太容易，可能导致不珍惜；真爱应保留对方说“不”的权利。
-- **反方**：珍惜程度取决于认真对待，而非获得爱的难易；将红线交给爱你的人比交给未知命运更可靠。
-- **正方**：使用超能力后，若相处不合适应放手，否则留下遗憾。
-- **反方**：若一开始就做好可能不合适的准备，则放手是爱的表现。
+- 正方提出“放手的爱”概念，认为爱应保留对方选择空间。反方回应：超能力可避免遗憾，掌握在自己手里比交给命运可靠。
+  &gt; “如果你今天爱的意思就是我明知道我是爱他的，但是你非要把他交给一个命运可能安排给他的渣男，这个时候我觉得你的放手就不是爱。”
+- 正方指出超能力可能用于控制、欺骗，类比PUA。反方回应：超能力机制未知，不一定是洗脑。
+  &gt; “你方天然就认为你一定是通过洗脑来获取他的爱。第一个问题，洗脑真的是爱吗？”
 ## 小节总结
-- **正方**：反方未能论证爱是自由意志的产物，洗脑式获取的爱并非真爱，而是占有。
-- **反方**：将红线交给爱你的人比交给未知命运更可靠，保留被爱者的选择空间。
+- 正方总结：对方预设“爱不能有自由意志”的前提，质疑洗脑能否换回真爱，强调珍惜取决于认真程度而非新鲜感。反方未在总结中回应。
+  &gt; “你方预设了一个前提，就是在爱或不爱这件事情上，人是不能有自由意志的。”
 # 结辩与评委点评
-- **正方结辩**：正方总结指出，反方未能论证爱是自由意志的产物，洗脑式获取的爱并非真爱，而是占有；真爱应保留对方说“不”的权利，超能力使爱来得太容易可能导致不珍惜。
-- **反方结辩**：反方强调爱是玄学，科学无法解释，超能力可改变自己或创造100%符合对方需求的条件，将红线交给爱你的人比交给未知命运更可靠。
-- **评委点评**：评委判定正方获胜，获得4分钟小结时间。</t>
+- **正方结辩**：正方总结对方暴露的问题，指出对方预设“爱不能有自由意志”的前提，质疑洗脑能否换回真爱，强调珍惜取决于认真程度而非新鲜感。正方认为超能力是洗脑，剥夺自由意志，类比强奸违背意志，因此不美好。
+- **反方结辩**：反方未在总结中明确结辩，但此前强调爱非自由意志产物，超能力机制未知，可能改变自己而非洗脑，超能力可拯救爱人，比月老可靠。
+- **评委点评**：主持人宣布正方在质询环节获胜，获得4分钟小结时间。</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>32.1</v>
+        <v>42.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12403/1264</t>
+          <t>12403/2288</t>
         </is>
       </c>
     </row>
@@ -9637,35 +9618,41 @@
       <c r="C27" t="inlineStr">
         <is>
           <t># 就诊概况
-患者为女性，年龄、职业未提及。2023年9月因腹痛确诊结肠癌并切除，术后行8期化疗；复查发现肝转移，行肝消融及乳腺结节切除，但腹膜转移可能切除不干净。后续化疗因肝功能不佳停用部分药物，停药3个月。2024年3月底复查发现肝、肺、腹膜转移，4月份PET-CT显示广泛转移，肠镜未见异常但PET显示有转移。本次就诊核心主诉为结肠癌术后转移，讨论后续全身治疗方案。
+本次为家属代述复诊，患者为结肠癌术后转移患者，未提供姓名、性别、年龄、职业等基本信息。核心主诉：2023年9月因腹痛突然发作、疼了一晚上，确诊结肠癌并接受切除手术，术后完成8期化疗；复查发现肝转移，从老家来北京做PET-CT；去年9月行肝消融和乳腺结节切除，当时存在腹膜转移，肠切除可能不干净；消融和结节切除后继续化疗，但仅第一次检查，后续因肝功能不行停用部分药物，中间停药3个月；3月底复查发现肝、肺、腹膜再次转移，4月份检查显示广泛转移。本次就诊要解决的问题：讨论后续全身治疗方案，特别是二次基因检测的必要性，以及除化疗、靶向治疗外是否有更有效的手段。
 # 病史与背景
-- **现病史**：2023年9月因腹痛（疼了一晚上）确诊结肠癌，行结肠癌切除手术，术后行8期化疗；复查发现肝转移，行肝消融及乳腺结节切除，但腹膜转移可能切除不干净；后续化疗因肝功能不佳停用部分药物，停药3个月；2024年3月底复查发现肝、肺、腹膜转移；4月份PET-CT显示广泛转移，肠镜未见异常但PET显示有转移。
-- **既往史**：患者多年来肠胃较弱，吃海鲜易上吐下泻。
-- **手术史**：结肠癌切除手术、肝消融、乳腺结节切除。
-- **近期用药**：化疗药物（具体药名未提及），因肝功能不佳停用部分药物。
+- **现病史**：2023年9月因腹痛突然发作，疼了一晚上，确诊结肠癌并接受切除手术；术后完成8期化疗。
+- **转移与治疗经过**：复查发现肝转移，从老家来北京做PET-CT；去年9月做肝消融和乳腺结节切除，当时存在腹膜转移，肠切除可能不干净；消融和结节切除后继续化疗，但仅第一次检查，后续因肝功能不行停用部分药物，中间停药3个月；3月底复查发现肝、肺、腹膜再次转移，4月份检查显示广泛转移。
+- **既往史**：患者多年来肠胃较弱，吃海鲜等易上吐下泻，一直认为肠胃比较弱；此前没有面对面贴的（原文表述，具体含义未明确）。
+- **近期检查**：上个月做肠镜显示无异常，但PET-CT显示有转移，医生认为可能是肠镜做得不好；患者背上也有一块，第一次看见，医生确认之前没有。
+- **近期用药**：化疗药物因肝功能不行停用部分药物，中间停药3个月；家属提到可服用四联康改善肠道问题。
 # 诊断与检查结果
-- **诊断结论**：结肠癌术后转移，累及肝、肺、腹膜。
-- **检查结果**：4月份PET-CT显示广泛转移；肠镜显示无异常，但PET显示有转移，医生认为可能是肠镜做得不好。
-- **基因检测**：建议进行基因检测（包括M2D等），可通过组织、血液、尿液、唾液进行。
-- **免疫评估**：建议进行免疫评估，了解免疫细胞状态。
+- **诊断结论**：结肠癌术后转移，目前存在肝、肺、腹膜广泛转移。
+- **检查结果**：PET-CT显示肝、肺、腹膜转移；肠镜显示无异常，但PET-CT显示有转移，医生认为可能是肠镜做得不好；4月份检查显示广泛转移。
+- **医生说明**：第一次基因检测可能不全面，建议做二次基因检测；基因检测可通过组织、血液、尿液、唾液进行；医生提到图片（可能指基因检测相关指标）在检查中非常常见，图片部分不高，图片可以提高，完全可以理解其区域图片；单机（可能指某种检测或药物）是基金的保护，因为图片主要是去修复，但修复机感觉没；成本在机场（可能指基因检测成本）非常高，在整个人类的社会医疗中非常高；现在的技术可以查到，尿液也可以查到，唾液整回来的话，以后诊断做基因检测；唾液要检测，给一条舌头填一填，看看这块如果出来可以了，那皮皮包已经出来了，这个没问题。
 # 治疗方案与医嘱
-- **检查安排**：建议进行基因检测（包括M2D等），可在肿瘤医院进行；建议进行免疫评估。
-- **治疗建议**：当前主要问题是全身系统治疗（化疗、靶向、免疫可联合使用），而非局部介入；若肿瘤增大至10公分或危及生命，才需考虑局部处理。
-- **用药说明**：因肝功能不佳，化疗药物停用部分，停药3个月。
-- **生活方式**：建议患者调整状态，提升免疫力。
+- **检查安排**：建议做二次基因检测，可通过组织、血液、尿液、唾液进行；建议在肿瘤医院做，大概有3个学科；第一次切片、第二次切片、第三次切片，一个一个号，从对讲中去找有没有可用的信息。
+- **治疗方向**：当前主要问题是全身治疗（系统治疗），而非局部介入；系统治疗包括化疗、靶向、免疫，可联合使用；免疫加靶向可能协同，如免疫加8000（可能指某种药物）；如果涨幅的10公分，房管的要命的，现在根本就小，要先系统治疗；系统治疗就要选药，选靶向，选免疫。
+- **生活方式**：建议患者调整状态，提升免疫力；可服用四联康改善肠道问题；让患者把状态调整好。
+- **用药说明**：化疗药物因肝功能不行停用部分药物，中间停药3个月；免疫加靶向可能协同，如免疫加8000（可能指某种药物）；另一个菲尼是结肠的三线药，是来推荐的，但我把它拿成加法了；免疫加8000，这时候机制我原来是低值，他去，但是他的助力和他的联合，从那个机制上是可能协同了，那协同就是1+1。
 | 药品名称 | 用法用量 | 注意事项 |
 | --- | --- | --- |
-| 未提及 | — | — |
+| 四联康 | — | — |
+# 病情说明与沟通
+- **医生解释**：基因检测很重要，第一次检测可能不全面，第二次检测可指导后续治疗；当前主要问题是全身治疗，而非局部介入；系统治疗包括化疗、靶向、免疫，可联合使用；免疫加靶向可能协同，如免疫加8000（可能指某种药物）；建议患者调整状态，提升免疫力。
+- **医生建议**：免疫加靶向可能协同，如免疫加8000（可能指某种药物）；建议患者调整状态，提升免疫力；让患者把状态调整好；医生提到免疫评估，但方案由家属定，看人家对不对。
+- **家属顾虑**：家属担心患者不知道扩散情况，不想做太多检查；医生认为当前应偏向患者自身状态调整，暂不增加额外检查。
+- **家属决定**：家属同意进行二次基因检测，并考虑全身治疗方案；家属询问是否需要再做核磁等检查，医生认为当前应关注患者状态，避免过度检查。
 # 复诊与预警信号
-未提及</t>
+- **观察变化**：患者今天早上查了血，医生建议关注患者自身免疫状态；医生提到免疫评估，但方案由家属定，看人家对不对。
+- **预警信号**：原文未提及需立即就医的预警症状。</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>26.5</v>
+        <v>53.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7063/897</t>
+          <t>7063/2040</t>
         </is>
       </c>
     </row>
@@ -9828,44 +9815,44 @@
       <c r="C28" t="inlineStr">
         <is>
           <t># 产品概况
-海尔洗衣机创新发布会于海尔洗衣机用户研发中心举行，主讲人介绍了专为中国用户阳台叠放痛点设计的洗干集成新物种迭代H2。该产品一体集成机身，解决洗烘套装叠放带来的震动安全隐患，高度降至167厘米，超薄机身可嵌入60厘米标准橱柜，全平不突出，并采用同向开门与无水盒设计。H2搭载多项创新技术：灵犀洗烘联动实现数据共享，洗涤结束前上桶提前15分钟主动预热；原创双擎热泵技术使大件烘干不缠绕；首次引入3D透视烘干，羽绒服和水洗被可一次烘透；升级精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗减少洗衣液残留；空净过滤系统去除衣物线屑和毛絮；三台变频电机降低洗涤、甩干、烘干全过程噪音。两款产品定价公布：10kg 3D透视烘干款12998元，10kg净净双擎热泵款10998元。
+海尔洗衣机创新发布会正式推出洗干集成新物种迭代H2，由海尔打造，专为中国家庭设计。核心Slogan为「纯净永无止境」。发布会指出，在欧洲滚筒洗衣机发源地，许多家庭有独立洗衣房，洗烘套装并排摆放；而在中国，80%的用户将洗烘套装叠放在阳台使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便。迭代H2专为客阳一体空间设计，目标人群是向往整洁有序新阳台的中国家庭，旨在通过一体集成机身与多项创新技术，解决阳台叠放痛点，让用户享受家的整洁有序。
 # 市场定位与目标用户
-目标人群为中国家庭，尤其是追求整洁有序新阳台、希望从漫长家务中解放出来的年轻人，以及养宠物、有宝宝的家庭。典型使用场景为客阳一体风格的阳台，用户在此休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间。市场背景：在欧洲滚筒洗衣机发源地，许多家庭有独立洗衣房，洗烘套装并排摆放；而在中国，80%的用户把洗烘套装叠放在阳台使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便。产品专为客阳一体空间设计，一体集成机身解决叠放带来的震动等安全隐患，高度降为167厘米，超薄机身嵌入60厘米标准橱柜，全平不突出，同向开门尊重使用习惯，无水盒设计无需手动倒水。
+目标人群为中国家庭，尤其是向往整洁有序新阳台、追求高效洗护与安静体验的用户，包括养宠物家庭和有宝宝的家庭。典型使用场景为客阳一体风格的阳台，年轻人常在阳台休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间。产品针对中国80%用户将洗烘套装叠放于阳台使用的习惯，与欧洲家庭独立洗衣房并排摆放形成对比。市场竞争策略以一体集成、平嵌超薄设计为核心，解决叠放带来的震动等安全隐患，并强调「真香的生活方式」。原文未提及同类产品或上代产品对比。
 # 核心卖点与技术参数
-## 集成设计
-- **一体集成机身**：专为客阳一体空间设计，解决洗烘套叠放带来的震动等安全隐患，高度降为167厘米，不用踮脚尖即可操作
-- **超薄平嵌**：超薄机身完美嵌入60厘米标准橱柜，全平不突出，让阳台更美观整洁
-- **同向开门**：尊重使用习惯，取放衣物流畅自如
-- **无水盒设计**：无需手动倒水
+## 一体集成设计
+- **一体集成机身**：专为客阳一体空间设计，解决洗烘套叠放带来的震动等安全隐患，高度降为167厘米，不用踮脚即可操作。
+- **超薄平嵌**：超薄机身完美嵌入60厘米标准橱柜，全平不突出，让阳台更美观整洁。
+- **同向开门**：尊重使用习惯，取放衣物流畅自如。
+- **无水盒设计**：无需手动倒水。
 ## 智慧互联
-- **灵犀洗烘联动**：H2独有的灵犀洗烘联动实现数据共享，让烘干和洗涤无缝连接，洗涤结束前上桶提前15分钟主动预热，缩短烘干时长
-- **智慧大脑**：H2全新升级的智慧大脑，利用中枢神经式的智能网络，让上下桶默契配合
+- **灵犀洗烘联动**：实现数据共享，让烘干和洗涤无缝连接，洗涤结束前上桶提前15分钟主动预热，缩短烘干时长。
+- **智慧大脑**：全新升级的智慧大脑，利用中枢神经式智能网络，让上下桶默契配合。
 ## 烘干技术
-- **原创双擎热泵技术**：大件烘干不缠绕
-- **3D透视烘干**：首次引入行业领先黑科技，羽绒服和水洗被可一次烘透，免去二次晾晒烦恼
+- **原创双擎热泵技术**：大件烘干不缠绕。
+- **3D透视烘干**：行业领先黑科技，羽绒服、水洗被可一次烘透，免去二次晾晒。
 ## 洗涤技术
-- **精华洗2.0**：升级精华洗2.0，激活洗衣液39分钟洗净一周衣物
-- **新鲜净水漂洗**：减少洗衣液残留，对残留泡沫敏感的人是福音
-## 健康护理
-- **空净过滤系统**：去除衣物线屑和毛絮，适合养宠物的家庭，洗衣无残留、干衣无毛絮，特别适合有宝宝的家庭
-- **三台变频电机**：洗涤、甩干、烘干全过程噪音低，享受安静陪伴时光
+- **精华洗2.0**：激活洗衣液，39分钟洗净一周衣物。
+- **新鲜净水漂洗**：减少洗衣液残留，对残留泡沫敏感的人是福音。
+## 健康与静音
+- **空净过滤系统**：去除衣物线屑和毛絮，适合养宠物家庭，洗衣无残留、干衣无毛絮，适合有宝宝的家庭。
+- **三台变频电机**：洗涤、甩干、烘干全过程噪音低。
 | 维度 | 本产品 | 上代/竞品 | 提升 |
 | --- | --- | --- | --- |
-| 集成设计 | 一体集成机身，高度167厘米，超薄嵌入60厘米标准橱柜，全平不突出，同向开门，无水盒设计 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决震动安全隐患，操作更便捷，阳台更美观整洁 |
-| 智慧互联 | 灵犀洗烘联动，数据共享，洗涤结束前上桶提前15分钟主动预热 | 洗烘套装貌合神离，无联动 | 烘干和洗涤无缝连接，缩短烘干时长 |
-| 烘干技术 | 原创双擎热泵技术，大件烘干不缠绕；首次引入3D透视烘干，羽绒服和水洗被一次烘透 | 未提及 | 免去二次晾晒烦恼 |
-| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物；新鲜净水漂洗减少洗衣液残留 | 未提及 | 洗衣更高效，减少残留 |
-| 健康护理 | 空净过滤系统去除线屑毛絮；三台变频电机降低噪音 | 未提及 | 适合养宠和有宝宝家庭，安静陪伴 |
+| 一体集成设计 | 一体集成机身，高度167厘米，超薄机身嵌入60厘米标准橱柜，全平不突出，同向开门，无水盒设计 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决叠放震动隐患，操作更便捷，外观更整洁 |
+| 智慧互联 | 灵犀洗烘联动，数据共享，上桶提前15分钟主动预热 | 洗烘套装貌合神离，无联动 | 烘干与洗涤无缝连接，缩短烘干时长 |
+| 烘干技术 | 原创双擎热泵技术，3D透视烘干，羽绒服、水洗被一次烘透 | 未提及 | 大件烘干不缠绕，免去二次晾晒 |
+| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗 | 未提及 | 洗衣更高效，减少洗衣液残留 |
+| 健康与静音 | 空净过滤系统去除线屑毛絮，三台变频电机 | 未提及 | 洗衣无残留、干衣无毛絮，全过程噪音低 |
 # 定价与发售信息
-10kg 3D透视烘干款定价12998元，10kg净净双擎热泵款定价10998元。定价策略：海尔为这款平嵌超薄产品拿出诚意满满的定价。发售时间、购买渠道与预售政策未提及。</t>
+10kg 3D透视烘干款定价12998元；10kg 净净双擎热泵款定价10998元。主讲人表示「为这款平嵌超薄产品拿出了诚意满满的定价」。发售时间、购买渠道与预售政策未提及。</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7311/1702</t>
+          <t>7311/1494</t>
         </is>
       </c>
     </row>
@@ -10068,90 +10055,97 @@
       <c r="C29" t="inlineStr">
         <is>
           <t># 全文摘要
-中共巢湖市银屏镇白母山村芦塘支部召开党员大会改选支部委员会。支部共有正式党员8名，因病请假1名，实到会有选举权党员7名，符合法定人数；银屏镇党委组织委员钱小丽应邀出席并代表镇党委提出三点意见。会议围绕换届选举展开，依次完成上届支部委员会工作报告审议、通过大会选举办法、支委候选人名单及监票计票人员名单、候选人竞职演说、无记名投票选举新一届支部委员和书记、支委分工等议程。大会选举发出并收回选票7张，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员；第一次支委会发出并收回选票3张，卢燕娇以3票当选党支部书记，辛东升负责组织宣传工作、杜军强负责纪检工作，最终结果以报镇党委批准为准。上届工作报告提及三年间新发展党员1名、收缴党费2640元上交上级党组织。
+中共巢湖市银屏镇白母山村芦塘支部召开党员大会改选支部委员会。支部共有党员8名，其中正式党员8名、有选举权，因病请假1名，实到会有选举权党员7名，符合法定人数；镇党委组织委员钱小丽应邀出席并代表镇党委提出三点意见。大会围绕换届选举展开，依次完成上届支委会工作报告、通过选举办法与候选人名单、通过监票计票人名单、候选人竞职演说、大会选举及第一次支委会选举书记与分工等议程。经无记名投票，卢艳娇、辛东升、杜军强当选为新一届支部委员会委员，卢艳娇当选为支部书记，辛东升负责组织宣传工作、杜军强负责纪检工作，选举结果以报镇党委批准为准。关键数字：支部党员8名、实到7名；上届收缴党费2640元；大会发出并收回选票7张，卢艳娇、杜军强各得6票、秦磊2票；支委会发出并收回选票3张，卢艳娇得3票当选。
 # 分段速览
 ## 00:00:13-00:02:03 大会开幕
-主持人宣布召开中共巢湖市银屏镇白母山村芦塘支部党员大会，改选支部委员会。支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到会有选举权党员7名，符合法定人数。银屏镇党委组织委员钱小丽应邀参加。主持人宣布大会开始，全体起立奏国歌。
-## 00:02:03-00:05:12 领导讲话与工作报告
-钱小丽代表镇党委提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。主持人代表上届支部委员会作工作报告，总结三年工作：加强思想政治建设和理论学习、抓好党支部建设、开展主题教育活动、党务公开、党风党纪教育；新发展党员1名，按规定收缴党费2640元上交上级党组织。报告指出存在问题：党建工作制度不够完善、党员主体意识尚需提高、党支部对党员教育管理监督不够深入。
+主持人宣布召开中共巢湖市银屏镇白母山村芦塘支部党员大会，改选支部委员会。支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到会有选举权党员7名，符合法定人数，可以开会。应邀参加今天会议的有银屏镇党委组织委员钱小丽同志。主持人宣布换届选举党员大会开始，全体起立奏国歌。
+## 00:02:03-00:05:12 镇党委讲话与上届工作报告
+钱小丽代表镇党委就做好换届选举工作提三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。主持人代表上届支部委员会作工作报告，总结三年工作：加强思想政治建设和理论学习、抓好党支部建设、开展主题教育活动、开展党务公开、抓好党风党纪教育；指出存在问题：党建工作制度不够完善、党员主体意识尚需提高、党支部对党员教育管理监督不够深入。
 ## 00:05:12-00:08:39 通过选举办法
-党员对工作报告无意见，鼓掌通过。杜军晓宣读党员大会选举办法草案，规定：选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；无记名投票，先差额选举委员再等额选举书记；实到会有选举权党员须超过应到会4/5方可选举；收回选票数等于或少于发出选票数选举有效；候选人得赞成票超过应到会选举人数半数方可当选。党员一致通过。
-## 00:08:39-00:10:43 通过候选人及工作人员名单
-杜军晓宣读镇党委批复，同意委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇，批复日期2019年10月12日。党员无不同意见，鼓掌通过。提议贾淑玲担任监票人，表决通过；宣布计票人员为黄婷丽、刘彩云。
+对工作报告进行讨论，党员表示满意，鼓掌通过。大会选举有6项议程。杜军晓宣读党员大会选举办法草案：选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；采用无记名投票方式，先差额选举委员再等额选举书记；有选举权正式党员须超过应到会党员4/5方可选举；候选人得赞成票超过应到会选举人数半数方可当选。经表决一致通过。
+## 00:08:39-00:10:43 通过候选人名单与工作人员名单
+杜军晓宣读镇党委批复，同意委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊，书记候选人预备人选卢艳娇，批复日期2019年10月12日。候选人名单经鼓掌通过。提议贾淑玲担任监票人，经表决通过；宣布计票人员为黄婷丽、刘彩云。
 ## 00:10:43-00:14:45 候选人竞职演说
-四位候选人依次演说。卢燕娇（1993年9月出生，2014年4月入党）承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强承诺担当桥梁纽带角色，为党员和群众服务；辛东升承诺群众有困难随叫随到，严格要求自己，完成上级任务；秦磊承诺有责任心、思想觉悟高，配合上级工作，不计较个人得失。
-## 00:14:45-00:21:17 大会选举新一届支部委员
-清点人数：应到会有选举权党员8名，因病请假1名，实到7名，达到应到会4/5，可以进行选举。检查票箱、分发选票、说明填写方法后投票。实到会有选举权党员7名，发出选票7张，收回7张，选举有效。计票结果：卢燕娇6票、杜军强6票、秦磊2票。卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。
+四位候选人依次发表竞职演说。卢艳娇介绍自己1993年9月出生、2014年4月入党，承诺加强支部建设、推动村集体经济发展、抓好民生工程。杜军强表示从事村委会工作，可担当桥梁纽带角色为党员和群众服务。辛东升承诺群众有困难随叫随到、严格要求自己、完成上级任务。秦磊强调责任心强、思想觉悟高，承诺配合上级工作、不计较个人得失。
+## 00:14:45-00:21:17 大会选举
+清点人数：应到会有选举权党员8名，因病请假1名，实到会7名，达到4/5，可以进行选举。监票人员检查并封好票箱，分发选票。主持人说明填写方法：赞成画圈、不赞成画叉、弃权不画符号，可另选他人；每张选票所选人数等于或少于应选人数为有效。投票后清点票数：发出选票7张、收回选票7张，选举有效。计票结果：卢艳娇6票、杜军强6票、秦磊2票。卢艳娇、辛东升、杜军强当选为新一届支部委员会委员。
 ## 00:21:17-00:28:42 第一次支委会选举书记及分工
-新当选委员召开第一次支委会，通过选举办法，规定等额选举书记1人，实到会委员须超过应到会4/5方可选举。主持人建议卢燕娇继续担任支部书记，无不同意见，鼓掌通过；提议辛东升担任监票人和计票人，表决通过。发出选票3张，收回3张，卢燕娇得3票当选新一届党支部书记。分工：辛东升负责组织宣传工作，杜军强负责纪检工作。
-## 00:28:42-00:29:56 宣布结果及闭幕
-主持人宣布选举结果：卢燕娇当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。新当选支委代表发言，承诺抓好学习、制度建设、完善基层党组织建设。大会圆满结束，全体起立奏国际歌。
+新当选委员召开第一次支部委员会全体会议，宣读选举办法草案：支部书记采用等额选举，实到会委员须超过应到会委员4/5方可选举。建议卢艳娇继续担任支部书记，经鼓掌通过；提议辛东升担任监票人和计票人，经表决通过。发出选票3张、收回选票3张，卢艳娇得3票当选为新一届党支部书记。分工：辛东升负责组织宣传工作，杜军强负责纪检工作。主持人宣布选举结果以报镇党委批准为准。
+## 00:28:42-00:29:56 新当选支委代表发言与大会闭幕
+新当选支委代表发言，承诺抓好支部学习工作、制度建设工作、完善基层党组织建设。主持人宣布中共巢湖市银屏镇白母山村芦塘支部委员会换届选举大会圆满结束，全体起立奏国际歌。
 # 要点梳理
-## 换届选举大会开幕及领导讲话
-- **参会人数**：支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到会有选举权党员7名，符合法定人数。
-- **出席人员**：银屏镇党委组织委员钱小丽应邀参加。
-- **钱小丽讲话**：代表镇党委提出三点意见——充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。
+## 换届选举大会开幕及镇党委讲话
+- **党员人数**：支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到会有选举权党员7名，符合法定人数，可以开会。
+- **参会人员**：银屏镇党委组织委员钱小丽应邀参加。
+- **钱小丽三点意见**：充分认识这次大会的重要意义；正确行使选举权，严格把握选举要求；服从大局，严格遵守选举纪律。
+- **钱小丽寄语**：希望新一届班子加强学习、提高素质，发挥战斗堡垒作用，带领全村党员和群众将白母山村建设得更加美好。
 ## 上届支部委员会工作报告
-- **工作成绩**：三年工作总结为五个方面——加强思想政治建设和理论学习、抓好党支部建设增强凝聚力、开展主题教育活动改进思想作风、开展党务公开推进党内民主、抓好党风党纪教育筑牢拒腐防变思想防线。
-- **具体数据**：新发展党员1名，按规定收缴党费2640元上交上级党组织。
-- **存在问题**：党建工作制度不够完善；党员主体意识尚需提高，个别党员干部顶推中心服务大局的意识不强；党支部对党员教育管理监督不够深入。
-- **报告审议**：党员对报告无意见，鼓掌通过。
-## 通过大会选举办法
-- **选举办法要点**：大会选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；候选人按姓氏笔画为序排列。
-- **选举方式**：采用无记名投票，先差额选举支部委员会委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布结果。
-- **有效条件**：参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；收回选票数等于或少于发出选票数选举有效，多于则无效。
-- **当选规则**：候选人得到赞成票数超过应到会选举人数半数方可当选；得票超过半数的候选人多于应选名额时以得票多少为序取足；最后几名票数相等时重新投票；超过半数候选人少于应选名额时不足名额在未过半数候选人中重新选举，接近应选名额可减少名额不再选举。
-- **选票填写**：赞成在候选人姓名上方空格画圈，不赞成画叉，弃权不画符号；另选他人在候选人后面空格写姓名并在其姓名上方画圈，只写姓名不画圈无效；每张选票所选人数等于或少于应选人数有效，超过无效。
+- **思想政治建设**：大力加强思想政治建设和理论学习，努力提高党员干部的思想理论水平。
+- **支部建设**：严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度；新发展党员1名，按规定收缴党费2640元上交上级党组织。
+- **主题教育活动**：认真开展“两学一做”学习教育常态化、制度化和“讲严立”专题警示教育活动。
+- **党务公开**：将年度工作计划、党风廉政建设、党费收缴等内容通过党内会议、公开栏等形式公开。
+- **党风党纪教育**：认真抓好党风党纪教育，筑牢拒腐防变的思想防线，落实党风廉政建设各项责任。
+- **存在问题**：党建工作制度不够完善；党员主体意识尚需进一步提高，个别党员干部围绕中心服务大局的意识不强；党支部对党员的教育管理监督不够深入。
+- **报告通过**：经讨论无意见，鼓掌通过。
+## 通过选举办法
+- **选举办法要点**：根据《中国共产党章程》和《中国共产党基层组织选举工作暂行条例》制定；选举支部委员会委员3名，候选人4名，差额不少于应选名额20%；候选人按姓氏笔画为序排列；采用无记名投票方式。
+- **选举步骤**：先差额选举支部委员会委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布结果。
+- **有效条件**：参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；收回选票数等于或少于发出选票数选举有效，多于发出选票数选举无效。
+- **当选条件**：候选人得到赞成票数超过应到会选举人数的半数方可当选；得票超过半数的候选人多于应选名额时以得票多少为序取足；最后几名得票相等时重新投票；超过半数候选人少于应选名额时，不足名额在未过半候选人中重新选举产生，接近应选名额也可减少名额不再选举。
+- **选票填写**：赞成在候选人姓名上方空格内画圈，不赞成画叉，弃权不画符号；另选他人在候选人后面空格内写姓名并画圈，只写姓名不画圈无效；每张选票所选人数等于或少于应选人数有效，超过无效。
 - **工作人员**：设监票人1名经大会表决通过，设选举工作人员2名由会议主持人指定；支部委员候选人不能担任监票人和工作人员。
-- **表决结果**：杜军晓宣读选举办法草案，党员大会一致通过。
-## 通过支委候选人名单
-- **镇党委批复**：银屏镇党委批复同意新一届支部委员会委员和书记候选人预备人选名单，批复日期2019年10月12日。
-- **候选人名单**：委员候选人预备人选4名——卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇。
-- **选举方式批复**：委员实行差额选举，差额1人；书记实行等额选举。
-- **表决结果**：党员无不同意见，鼓掌通过候选人名单。
-## 通过选举工作人员名单
-- **监票人**：提议贾淑玲担任监票人，经表决一致通过。
-- **计票人**：宣布计票人员为黄婷丽、刘彩云。
+- **表决结果**：无不同意见，一致通过。
+## 通过候选人名单
+- **镇党委批复**：中共巢湖市银屏镇白母山村芦塘支部委员会组成人员候选人预备人选名单收悉，经研究同意；委员实行差额选举差额1人，书记实行等额选举；批复日期2019年10月12日。
+- **委员候选人预备人选4名**：卢燕娇、辛东升、杜军强、秦磊。
+- **书记候选人预备人选**：卢艳娇。
+- **表决结果**：无不同意见，鼓掌通过。
+## 通过监票人、计票人名单
+- **监票人**：贾淑玲，经表决一致通过。
+- **计票人**：黄婷丽、刘彩云，由主持人宣布。
 ## 候选人竞职演说
-- **卢燕娇**：1993年9月出生，2014年4月加入中国共产党；承诺进一步加强支部建设，落实三会一课、组织生活会和民主评议党员等基本制度，结合两学一做学习教育常态化制度化开展不忘初心、牢记使命主题教育；进一步推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领和帮扶帮带作用；进一步抓好各项民生工程落实，把群众利益作为工作首要职责、群众满意度作为衡量工作标准。
-- **杜军强**：从事村委会工作，平时与各类人群有工作接触；承诺如当选可更好担当桥梁纽带角色，向基层党员传达广大党员和群众的利益诉求，为党员和群众服务。
+- **卢艳娇**：1993年9月出生，2014年4月加入中国共产党；承诺进一步加强支部建设，落实“三会一课”、组织生活会和民主评议党员等基本制度，扎实开展“不忘初心、牢记使命”主题教育；进一步推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领和帮扶帮带作用；进一步抓好各项民生工程落实，把群众利益作为工作首要职责、群众满意度作为衡量工作标准。
+- **杜军强**：从事村委会工作，平时与各类人群有工作接触；承诺担当基层党组织与党员群众之间的桥梁纽带角色，向基层党员传达广大党员和群众的利益诉求，为党员和群众服务。
 - **辛东升**：承诺群众有困难随叫随到；严格要求自己做合格党员干部，不该吃的饭不吃、不该拿的钱不拿、不该做的事不做；圆满完成上级党组织分配的各项任务。
-- **秦磊**：竞选有利条件为有较强责任心、能认真参加支部组织的理论学习、不折不扣完成组织交给的任务；有较高思想觉悟，利用业余时间学习；承诺配合上级和各项工作，全体党员团结一心，不计较个人得失，当一名合格的支部委员。
-## 大会选举新一届支部委员
+- **秦磊**：强调有较强责任心，能认真参加支部组织的理论学习，不折不扣完成组织交给的任务；有较高思想觉悟，利用业余时间学习；承诺配合上级和各项工作，全体党员团结一心、听从大局、不计较个人得失，当一名合格的支部委员。
+## 大会选举及结果
 - **清点人数**：应到会有选举权党员8名，因病请假1名，实到会7名，达到应到会有选举权党员人数的4/5，可以进行选举。
-- **选票发放与回收**：发出选票7张，收回选票7张，选举有效。
-- **计票结果**：卢燕娇6票，杜军强6票，秦磊2票。
-- **当选结果**：卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。
+- **选票发放**：监票人员检查并封好票箱，发出选票7张。
+- **填写说明**：赞成画圈、不赞成画叉、弃权不画符号；投不赞成票的可另选他人，弃权不能另选他人；每张选票所选人数等于或少于应选人数为有效票，多于为无效票；一律用钢笔填写。
+- **投票与清点**：监票人、计票人先投票，全体党员依次投票；实到会有选举权党员7名，发出选票7张，收回选票7张，选举有效。
+- **计票结果**：卢艳娇6票，杜军强6票，秦磊2票。
+- **当选结果**：卢艳娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。
 ## 第一次支委会选举书记及分工
-- **选举办法**：支委会第一次全体会议选举产生支部书记1人；选举工作由上届支部委员会委托一名新当选委员主持；书记候选人建议名单由上届支委会根据镇党委批复提交新支委会酝酿，根据多数委员意见确定正式候选人；采用无记名投票，等额选举；实到会委员须超过应到会委员4/5方可选举；候选人得赞成票超过实到会委员半数当选。
-- **书记候选人**：主持人介绍卢燕娇工作认真负责，上届支委会在其带领下各项工作取得较好成绩，建议继续由卢燕娇担任支部书记；无不同意见，鼓掌通过。
-- **工作人员**：提议辛东升担任监票人和计票人，表决通过。
-- **选举结果**：发出选票3张，收回选票3张，卢燕娇得3票当选新一届党支部书记。
+- **选举办法要点**：根据《中国共产党章程》《中国共产党基层组织选举工作暂行条例》制定；选举产生支部书记1人；支部书记采用等额选举；实到会委员必须超过应到会委员的4/5方可选举；收回选票等于或少于发出选票选举有效；候选人得到赞成票超过实到会委员半数当选；设监票人1名由会议主持人在非书记候选人中提名，计票人由会议主持人指定。
+- **书记候选人建议名单**：建议卢艳娇继续担任支部书记，经鼓掌通过。
+- **监票人、计票人**：提议辛东升担任监票人和计票人，经表决一致通过。
+- **选举结果**：发出选票3张，收回选票3张，卢艳娇得3票，当选为新一届党支部书记。
 - **委员分工**：辛东升负责组织宣传工作，杜军强负责纪检工作。
-## 宣布选举结果及闭幕
-- **选举结果宣布**：卢燕娇当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。
-- **新当选支委代表发言**：承诺抓好支部学习工作，争创学习型支部，组织开展不忘初心、牢记使命主题教育；抓好支部制度建设工作，争创制度型支部；完善基层党组织建设，争创服务型支部，严格按照中国共产党党支部工作条例（试行）加强支部建设，发挥战斗堡垒和党员先锋模范作用。
-- **大会闭幕**：大会完成各项任务，全体起立奏国际歌，换届选举大会圆满结束。
+## 大会闭幕
+- **选举结果宣布**：卢艳娇当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。
+- **新一届支委代表发言**：承诺抓好支部学习工作，认真组织开展“不忘初心、牢记使命”主题教育；抓好支部制度建设工作，增强党支部凝聚力、战斗力；完善基层党组织建设，严格按照《中国共产党党支部工作条例（试行）》加强支部建设，发挥战斗堡垒和党员先锋模范作用，更好服务基层服务群众。
+- **大会结束**：宣布换届选举大会圆满结束，全体起立奏国际歌。
 ## 结论与决定
-- **通过党员大会选举办法**：党员大会一致表决通过。
-- **通过支委候选人名单**：卢燕娇、辛东升、杜军强、秦磊为委员候选人，卢燕娇为书记候选人，鼓掌通过。
-- **通过选举工作人员名单**：贾淑玲任监票人，黄婷丽、刘彩云任计票人，表决通过。
-- **新一届支部委员会当选**：卢燕娇、辛东升、杜军强当选为支部委员会委员。
-- **新一届党支部书记当选**：卢燕娇当选为党支部书记，等额选举得3票，最终结果以报镇党委批准为准。
-- **委员分工确定**：辛东升负责组织宣传工作，杜军强负责纪检工作。
+- **通过上届支部委员会工作报告**：经讨论无意见，鼓掌通过。
+- **通过党员大会选举办法**：无不同意见，一致通过。
+- **通过支委候选人名单**：卢燕娇、辛东升、杜军强、秦磊，经鼓掌通过。
+- **通过监票人、计票人名单**：监票人贾淑玲，计票人黄婷丽、刘彩云，经表决一致通过。
+- **选举产生新一届支部委员会委员**：卢艳娇、辛东升、杜军强当选。
+- **选举产生新一届党支部书记**：卢艳娇得3票当选，最终结果以报镇党委批准为准。
+- **支部委员分工**：辛东升负责组织宣传工作，杜军强负责纪检工作。
 ## 行动项与分工
-- **辛东升**：负责支部组织宣传工作。
-- **杜军强**：负责支部纪检工作。
-- **新一届支委会**：抓好支部学习工作，组织开展不忘初心、牢记使命主题教育；抓好支部制度建设工作；完善基层党组织建设，按中国共产党党支部工作条例（试行）加强支部建设。
-- **选举结果报送**：选举结果报镇党委批准（原文明确最终结果以报镇党委批准为准，未明确具体报送时限与责任人）。</t>
+- **辛东升**：负责新一届支部组织宣传工作。
+- **杜军强**：负责新一届支部纪检工作。
+- **新一届支委**：抓好支部学习工作，争创学习型支部；抓好支部制度建设工作，争创制度型支部；完善基层党组织建设，争创服务型支部。
+- **选举结果报送**：选举结果报镇党委批准。</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>64.3</v>
+        <v>62.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8414/4684</t>
+          <t>8414/5065</t>
         </is>
       </c>
     </row>
@@ -10288,131 +10282,129 @@
       <c r="C30" t="inlineStr">
         <is>
           <t># 报告概况
-国务院总理代表国务院向全国人民代表大会作《政府工作报告》，请予审议，并请全国政协委员提出意见。报告回顾2023年工作，提出2024年经济社会发展总体要求、主要预期目标和政府工作任务。2023年，面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务，全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元、增长5.2%，城镇新增就业1244万人，粮食产量1.39万亿斤再创历史新高。2024年是中华人民共和国成立75周年、实现“十四五”规划目标任务的关键一年，报告坚持稳中求进工作总基调，提出国内生产总值增长5%左右等主要预期目标，部署大力推进现代化产业体系建设、加快发展新质生产力等十个方面政府工作任务，基调积极进取、务实为民。
+本报告为国务院总理代表国务院在十四届全国人大二次会议上所作的《政府工作报告》，发布单位为国务院，报告期间涵盖2023年工作回顾与2024年工作部署。报告核心主题是全面贯彻党的二十大精神，坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，着力推动高质量发展，以中国式现代化全面推进强国建设、民族复兴伟业。报告整体基调务实进取，既客观总结2023年经济社会发展成绩与面临的困难挑战，又明确2024年主要预期目标和政策取向，部署全年政府工作任务。2023年国内生产总值超过126万亿元，增长5.2%，城镇新增就业1244万人；2024年主要预期目标为国内生产总值增长5%左右，城镇新增就业1120万人。
 # 核心政策
-## 2024年经济社会发展总体要求与政策取向
-- **总体要求**：坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，加快构建新发展格局，着力推动高质量发展，全面深化改革开放，推动高水平科技自立自强，加大宏观调控力度，统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全。
-- **政策基调**：坚持稳中求进、以进促稳、先立后破，多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施；在转方式、调结构、提质量、增效益上积极进取，强化宏观政策逆周期和跨周期调节。
-- **形势研判**：今年我国发展面临的环境仍是战略机遇和风险挑战并存，**有利条件强于不利因素**；实现今年预期目标并非易事，需要政策聚焦发力、工作加倍努力、各方面齐心协力。
-## 2024年主要预期目标
-- **经济增长**：国内生产总值增长**5%左右**。
-- **就业**：城镇新增就业**1120万人**，城镇调查失业率**5.5%左右**。
-- **物价**：居民消费价格涨幅**3%左右**。
-- **收入**：居民收入增长和经济增长同步。
-- **国际收支**：国际收支保持基本平衡。
-- **粮食安全**：粮食产量**1.3万亿斤以上**。
-- **能耗**：单位国内生产总值能耗降低**2.5%左右**。
-- **生态**：生态环境质量持续改善。
-## 财政政策
-- **赤字率**：拟按**3%**安排，赤字规模**4.06万亿元**。
-- **支出规模**：一般公共预算支出规模**28.5万亿元**。
-- **地方政府专项债券**：拟安排**3.9万亿元**。
-- **超长期特别国债**：为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，**今年先发行10000亿元**。
-- **支出结构优化**：大力优化支出结构，强化国家重大战略任务和基本民生财力保障；中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜；省级财政要推动财力下沉，兜牢基层`三保`底线。
-- **过紧日子**：各级政府要习惯过紧日子，切实把财政资金用在刀刃上、用出实效。
-## 货币政策
-- **总体取向**：稳健的货币政策要灵活适度、精准有效，保持流动性合理充裕。
-- **融资与货币供应**：社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配。
-- **融资成本**：促进社会综合融资成本稳中有降。
-- **资本市场与汇率**：增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。
-## 宏观政策取向一致性
-- **政策协调配合**：围绕发展大局加强政策协调配合，把非经济性政策纳入宏观政策取向一致性评估，确保同向发力、形成合力。
-- **政策制定程序**：各地区各部门制定政策要认真听取和吸纳各方面意见，涉企政策要注重与市场沟通、回应企业关切，营造稳定、透明、可预期的政策环境。
-## 2024年政府工作任务总体部署
-- **工作总纲**：深入贯彻习近平经济思想，集中精力推动高质量发展，强化系统观念，把握和处理好重大关系，以更大的决心和力度深化改革开放，持续激发和增强社会活力。
-- **任务框架**：党中央对今年工作作出全面部署，涵盖大力推进现代化产业体系建设、深入实施科教兴国战略、着力扩大国内需求、坚定不移深化改革、扩大高水平对外开放、更好统筹发展和安全、坚持不懈抓好三农工作、推动城乡融合和区域协调发展、加强生态文明建设、切实保障和改善民生等十个方面。
+## 核心政策
+### 2024年发展主要预期目标
+- **国内生产总值增长5%左右**，城镇新增就业**1120万人**，城镇调查失业率**5.5%左右**
+- **居民消费价格涨幅3%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡
+- **粮食产量1.3万亿斤以上**，单位国内生产总值能耗降低**2.5%左右**，生态环境质量持续改善
+### 财政政策
+- 积极的财政政策适度加力、提质增效，赤字率拟按**3%**安排，赤字规模**4.06万亿元**
+- 一般公共预算支出规模**28.5万亿元**，拟安排地方政府专项债券**3.9万亿元**
+- 为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，今年先发行**10000亿元**
+- 中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜；省级财政推动财力下沉，兜牢基层`三保`底线
+- 各级政府要习惯过紧日子，切实把财政资金用在刀刃上
+### 货币政策
+- 稳健的货币政策灵活适度、精准有效，保持流动性合理充裕
+- 社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配，促进社会综合融资成本稳中有降
+- 增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定
+- 加强宏观政策取向一致性评估，把非经济性政策纳入评估范围，确保同向发力、形成合力；涉企政策注重与市场沟通，回应企业关切，营造稳定、透明、可预期的政策环境
+### 产业与科技政策
+- 实施`制造业重点产业链高质量发展行动`，着力补齐短板、拉长长板、锻造新板，推动传统产业高端化、智能化、绿色化转型
+- 促进中小企业`专精特新`发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌
+- 巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资
+- 制定支持数字经济高质量发展政策，开展`人工智能+`行动，实施`制造业数字化转型行动`，大力推动数据开发开放和流通使用
+- 制定实施`教育强国建设规划纲要`，开展`基础教育扩优提质行动`，加快建设中国特色世界一流的大学和优势学科
+- 充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发
+- 强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护
+- 实施更加积极、更加开放、更加有效的人才政策，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系
+### 扩大内需政策
+- 从增加收入、优化供给、减少限制性措施等方面综合施策促进消费稳定增长，实施`数字消费`、`绿色消费`、`健康消费`促进政策
+- 鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费，推动养老、育幼、家政等服务扩容提质
+- 发挥政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施`十四五`规划重大工程项目
+- 着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为
+### 改革开放政策
+- 深入实施`国有企业改革深化提升行动`，全面落实促进民营经济发展壮大的意见及配套举措，实施`降低物流成本行动`，健全防范化解拖欠企业账款长效机制
+- 加快全国统一大市场建设，专项治理地方保护、市场分割、招商引资不当竞争等突出问题
+- 谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革
+- 推动外贸稳规模优结构，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，出台服务贸易、数字贸易创新发展政策
+- **全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇
+- 深入实施`自贸试验区提升战略`，抓好支持高质量共建`一带一路`八项行动落实落地，稳步推进重大项目合作，实施一批`小而美`民生项目，加快建设西部陆海新通道
+- 与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革
+### 风险防范与安全政策
+- 优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实`一揽子化债方案`，稳妥推进中小金融机构风险处置
+- 加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求
+- 建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力
+- 全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定
+### 三农与区域协调政策
+- 学习运用`千村示范、万村整治`工程经验，推动乡村全面振兴；稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平
+- 加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度
+- **启动第二轮土地承包到期后再延长30年整省试点**，深入实施乡村建设行动，持续改善农村人居环境
+- 把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善`人地钱挂钩`政策，推动未落户常住人口平等享受城镇基本公共服务
+- 深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展
+### 生态文明政策
+- 深入实施`空气质量持续改善行动计划`，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好`三北`工程三大标志性战役
+- 完善生态产品价值实现机制，推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，推动废弃物循环利用产业发展，建设美丽中国先行区
+- 积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系
+### 民生保障政策
+- 突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过**1170万人**，强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作
+- 多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收
+- **居民医保人均财政补助标准提高30元**，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新
+- **城乡居民基础养老金月最低标准提高20元**，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设
+- 健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢
+- 创新实施`文化惠民工程`，大力发展文化产业，推动全民健身活动广泛开展
+- 贯彻总体国家安全观，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；坚持和发展新时代`枫桥经验`，推进矛盾纠纷预防化解，推动信访工作法治化
+# 重点工作
 ## 现代化产业体系建设
-- **产业链供应链优化升级**：保持工业经济平稳运行，实施`制造业重点产业链高质量发展`行动，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的`中国制造`品牌。
-- **战略性新兴产业**：促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
-- **数字经济**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展`人工智能+`行动，实施`制造业数字化转型`行动，大力推动数据开发开放和流通使用。
-## 科教兴国战略
-- **高质量教育体系**：全面贯彻党的教育方针，制定实施`教育强国建设规划纲要`，落实立德树人根本任务，开展`基础教育扩优提质`行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
-- **高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发；强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作。
-- **人才政策**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
-## 扩大国内需求
-- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
-- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施`十四五`规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
-## 深化改革
-- **激发各类经营主体活力**：不断完善落实`两个毫不动摇`的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施`国有企业改革深化提升`行动，全面落实促进民营经济发展壮大的意见及配套举措，实施`降低物流成本`行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投。
-- **全国统一大市场**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
-- **财税金融改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
-## 扩大高水平对外开放
-- **外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
-- **加大吸引外资力度**：**全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施`自贸试验区提升`战略，打造对外开放新高地。
-- **共建一带一路**：推动高质量共建`一带一路`走深走实，抓好支持高质量共建`一带一路`八项行动落实落地，稳步推进重大项目合作，实施一批`小而美`民生项目，加快建设西部陆海新通道。
-- **多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
-## 统筹发展和安全
-- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案；稳妥推进一些地方的中小金融机构风险处置。
-- **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
-- **重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
-## 三农工作与乡村全面振兴
-- **粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平；各地区都要扛起保障国家粮食安全责任。
-- **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
-- **农村改革与发展**：启动**第二轮土地承包到期后再延长30年整省试点**，促进农民增收，壮大乡村富民产业；深入实施`乡村建设`行动，持续改善农村人居环境，建设宜居宜业和美乡村。
-## 城乡融合与区域协调发展
-- **新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务；新型城镇化要处处体现以人为本。
-- **区域协调发展**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
-## 生态文明建设
-- **生态环境综合治理**：深入践行`绿水青山就是金山银山`理念，协同推进降碳、减污、扩绿、增长；深入实施`空气质量持续改善行动计划`，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好`三北`工程三大标志性战役，完善生态产品价值实现机制。
-- **绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
-- **碳达峰碳中和**：积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
-## 保障和改善民生
-- **稳就业促增收**：突出就业优先导向，加大促就业专项政策力度；**预计今年高校毕业生超过1170万人**，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
-- **医疗卫生服务**：居民医保人均财政补助标准**提高30元**；深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展`健康中国`行动和爱国卫生运动。
-- **社会保障**：城乡居民基础养老金月最低标准**提高20元**，继续提高退休人员基本养老金；加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢。
-- **文化体育事业**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施`文化惠民工程`，大力发展文化产业，推动全民健身活动广泛开展。
-- **国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代`枫桥经验`，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
-# 重点工作
-## 大力推进现代化产业体系建设，加快发展新质生产力
 - **推动产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌。
 - **促进战略性新兴产业融合集群发展**：巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
-- **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展“人工智能+”行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
-## 深入实施科教兴国战略，强化高质量发展的基础支撑
+- **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展人工智能+行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
+## 科教兴国战略
 - **加强高质量教育体系建设**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务，开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
 - **加快推动高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发；强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作，营造具有全球竞争力的开放创新生态。
 - **全方位培养用好人才**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
-## 着力扩大国内需求，推动经济实现良性循环
-- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
-- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施“十四五”规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
-## 坚定不移深化改革，增强发展内生动力
-- **激发各类经营主体活力**：不断完善落实“两个毫不动摇”的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投。
+## 扩大国内需求
+- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大众消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
+- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施十四五规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
+## 深化改革
+- **激发各类经营主体活力**：不断完善落实两个毫不动摇的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投。
 - **加快全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
 - **推进财税、金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
-## 扩大高水平对外开放，促进互利共赢
+## 扩大高水平对外开放
 - **推动外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
 - **加大吸引外资力度**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施自贸试验区提升战略，打造对外开放新高地。
-- **推动高质量共建“一带一路”走深走实**：抓好支持高质量共建“一带一路”八项行动落实落地，稳步推进重大项目合作，实施一批“小而美”民生项目，加快建设西部陆海新通道。
+- **推动高质量共建一带一路走深走实**：抓好支持高质量共建一带一路八项行动落实落地，稳步推进重大项目合作，实施一批小而美民生项目，加快建设西部陆海新通道。
 - **深化多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
-## 更好统筹发展和安全，有效防范化解重点领域风险
-- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案；稳妥推进一些地方的中小金融机构风险处置。
+## 统筹发展和安全
+- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
 - **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
 - **加强重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
-## 坚持不懈抓好“三农”工作，扎实推进乡村全面振兴
+## 三农工作与乡村全面振兴
 - **加强粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平。
-&gt; 各地区都要扛起保障国家粮食安全责任。我们这样一个人口大国，必须始终把饭碗牢牢端在自己手上。
-- **毫不放松巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
+&gt; 我们这样一个人口大国，必须始终把饭碗牢牢端在自己手上。
+- **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
 - **稳步推进农村改革发展**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业；深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
-## 推动城乡融合和区域协调发展，大力优化经济布局
+## 城乡融合与区域协调发展
 - **积极推进新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
 - **提高区域协调发展水平**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
-## 加强生态文明建设，推进绿色低碳发展
-- **推动生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好“三北”工程三大标志性战役，完善生态产品价值实现机制。
+## 生态文明建设
+- **推动生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好三北工程三大标志性战役；完善生态产品价值实现机制，充分调动各方面保护和改善生态环境的积极性。
 - **大力发展绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
 - **积极稳妥推进碳达峰碳中和**：扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
-## 切实保障和改善民生，加强和创新社会治理
+## 保障和改善民生
 - **多措并举稳就业促增收**：突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
 - **提高医疗卫生服务能力**：居民医保人均财政补助标准提高30元；深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展健康中国行动和爱国卫生运动。
 - **加强社会保障**：城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金；加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢。
 - **丰富人民群众精神文化生活**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。
-- **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代“枫桥经验”，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。</t>
+- **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代枫桥经验，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
+## 政府自身建设
+- **深入推进依法行政**：严格遵守宪法法律，自觉接受同级人大及其常委会的监督，自觉接受人民政协的民主监督，自觉接受社会和舆论监督，加强审计监督，坚持科学民主依法决策，支持工会、共青团、妇联等群团组织更好发挥作用。
+- **纵深推进党风廉政建设和反腐败斗争**：发扬自我革命精神，政府工作人员要遵守法纪、廉洁修身、勤勉尽责，干干净净为人民服务。
+- **全面提高行政效率**：深入推进政府职能转变，不断提高执行力和公信力，在抓落实上切实做到不折不扣、雷厉风行、求真务实；提高政务服务水平，坚决纠正形式主义、官僚主义，持续为基层和企业减负。
+## 民族、宗教、侨务与国防外交
+- **民族宗教侨务工作**：以铸牢中华民族共同体意识为主线，促进各民族广泛交往、交流、交融；坚持党的宗教工作基本方针，深入推进我国宗教中国化；加强和改进侨务工作，汇聚起海内外中华儿女共同致力民族复兴的磅礴力量。
+- **国防和军队建设**：深入贯彻习近平强军思想，贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全面深入贯彻军委主席负责制，打好实现建军一百年奋斗目标攻坚战；全面加强练兵备战，坚定捍卫国家主权、安全、发展利益；抓好军队建设十四五规划执行，加快实施国防发展重大工程；各级政府要大力支持国防和军队建设，巩固发展军政军民团结。
+- **港澳台工作**：继续全面准确、坚定不移贯彻一国两制、港人治港、澳人治澳、高度自治的方针，坚持依法治港治澳，落实爱国者治港、爱国者治澳的原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局；坚持贯彻新时代党解决台湾问题的总体方略，坚持一个中国原则和九二共识，坚决反对台独分裂和外来干涉，推动两岸关系和平发展，深化两岸融合发展，增进两岸同胞福祉。
+- **外交工作**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体。</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>58.4</v>
+        <v>53.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9903/8888</t>
+          <t>9903/7597</t>
         </is>
       </c>
     </row>
@@ -11247,90 +11239,101 @@
       <c r="C31" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-杭州医学院检验医学院、生物工程学院通过B站、微博、抖音等平台开展专场直播，由学院党委书记、副院长宋宝峰副教授面向考生及家长介绍医学技术专业硕士点的招生情况与培养特色。该学位点于2024年获批，由检验医学院、生物工程学院（合署办公）牵头，联合医学影像学院、康复学院、信息工程学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向。直播围绕学位点基本情况、学科建设与优势、研究方向、师资队伍、培养与就业、2026年招考计划及复试安排等展开，并现场解答考生关于就业前景、初试科目、跨专业报考等疑问。整体基调为积极推介，强调学科实力与就业竞争力，欢迎考生报考。
+杭州医学院检验医学院、生物工程学院举办专场招生直播，由学院党委书记、副院长宋宝峰做客直播间，面向考生及家长介绍医学技术专业硕士点的招生情况与培养特色。沟通旨在帮助广大考生全面了解2026年研究生招生信息，重点围绕学位点基本情况、学科优势、研究方向、师资队伍、培养与就业去向及招考计划等内容进行宣讲，并现场解答考生关于就业前景、初试科目、跨专业报考等疑问。整体宣讲基调积极，宋宝峰对学位点的学科竞争力与就业前景表达了充分信心，并诚挚欢迎考生报考。
 # 核心信息与数据
 ## 学位点基本情况
 - **学位点获批**：医学技术专业硕士点于2024年获批，为新增学位点。
 - **共建学院**：由检验医学院、生物工程学院（合署办公）牵头，医学影像学院、康复学院、信息工程学院共建，共5个学院承担培养工作。
 - **专业方向**：聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向，其中检验技术细分为医检和卫检两个方向。
-## 2025年招生情况
-- **录取人数**：2025年录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
-## 学科建设与科研平台
+- **2025年招生**：录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
+## 学科建设与优势
 - **学科层次**：医学技术于2023年获批浙江省一流学科B类。
-- **科研项目与经费**：近五年获国家级基金项目19项、省鉴定领先项目1项；纵向科研经费1300万元，横向合作课题经费2200多万元。
-- **科研获奖**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
+- **科研项目与经费**：近五年获国家级基金项目19项、省鉴定领先项目1项，纵向科研经费1300万，横向合作课题经费2200多万。
+- **科研奖项**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
 - **课程与专业建设**：建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
-- **省级科研平台**：建有省生物标志物与器官诊断转化重点实验室（2024年获批）、检验诊断关键技术研究室（2022年）、康复模块和机器人国际联合实验室（2023年）、省实验室和安全培训基地、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、浙江省神经系统疾病数字化装备研发重点实验室（2024年）等。
-## 学科优势
-- **体外诊断领域**：疫情期间与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册；为中华医学会检验医学分会教育学组组长单位、卫生高新技术公司实体开发基地。
-- **医学影像技术方向**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向，建有国家级本科专业建设点、省医学重点学科、省临床放射质控中心、国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地等平台。
+- **省级科研平台**：建有省生物标志物与器官诊断转化重点实验室、检验诊断关键技术研究室、康复模块和机器人国际联合实验室、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、省神经系统疾病数字化装备研发重点实验室等。
+- **体外诊断领域**：疫情期间与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册。
+- **医学影像技术方向**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向，建有国家级本科专业建设点、省医学重点学科、省临床放射质控中心、国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地。
 - **康复治疗方向**：依托省人民医院康复医学科，为省内综合医院中建科最早、人才最齐、技术最先进、设备最先进、社会效益最佳的康复医学科之一。
-- **智能医学工程方向**：聚焦阿尔茨海默病智能预警数字生物标志物，居国际领跑水平；为浙江省中医药重点学科、老年助浴疾病数字器械医疗器械浙江省中心、智能医学前沿交叉学院。
+- **智能医学工程方向**：聚焦阿尔茨海默病智能预警生物标志物（数字生物标志物），居国际领跑水平，为浙江省中医药重点学科、老年助浴疾病数字器械医疗器械浙江省中心、智能医学前沿交叉学院。
 ## 主要研究方向
-- **医学检验技术方向**：负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制、新发突发传染病新型生物标志物筛选及致病机制、重大疾病体外诊断检测技术、新型药物系统治疗难治性疾病、神经免疫与再生五个方向；团队承担多项国家级和省部级项目，在线粒体氧化磷酸化功能改变与线粒体相关疾病、新冠病毒快速检测试剂方面取得突破，发表高水平论文百余篇。
-- **卫生检验检疫方向**：负责人金大志研究员，聚焦新发突发传染病病原体检测检验新技术开发（艰难梭菌致病机制、耐药机制、基因组进化及小分子药物开发）和卫生检验技术研究；获省科技进步二等奖、三等奖各1项，省医药卫生科技进步一等奖1项、二等奖2项、三等奖1项，发表中科院一二区论文85篇，主编专业教材12部、主审7部。
-- **医学影像技术方向**：负责人徐秀芳教授，研究多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位四个方向；主持国家自然科学基金3项、省部级项目20多项，获全国优秀教材二等奖1项。
-- **康复治疗方向**：负责人倪湘明教授（附属人民医院），研究康复技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病五个方向；团队获国家级课题23项、省级课题23项，省科技进步三等奖2项、省医药卫生科技进步二等奖2项，国家发明专利和实用新型专利77项，主编专业书籍、主审教材8部、参编书籍40多部。
-- **智能医学工程方向**：负责人李海教授，聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病（阿尔茨海默病、帕金森病、抑郁症、自闭症等）智能诊断五个方向；主持参与国家级项目3项、省部级重点研发计划及200万元以上重大设计项目，与中国人民解放军总医院、浙一医院、日本文化研究所等单位开展合作；与浙大联合研制的阿尔茨海默病数字预警仪已申报二类医疗器械。
+- **医学检验技术方向**：负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制、新发突发传染病标志物筛选及致病机制、重大疾病体外诊断检测技术、新型药物系统治疗难治疾病、神经免疫与再生研究。
+- **卫生检验检疫方向**：负责人金大志研究员，聚焦新发突发传染病病原体检测检验新技术方法开发，包括艰难梭菌致病机制、耐药机制、基因组进化及小分子药物开发，以及卫生检验技术研究。
+- **医学影像技术方向**：负责人徐秀芳教授，研究方向为多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位。
+- **康复治疗方向**：负责人倪湘明教授（附属人民医院），研究方向为康复技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医结合康复治疗神经系统疾病。
+- **智能医学工程方向**：负责人李海教授，研究方向为脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病智能诊断。
+- **吕建新教授团队**：承担国家级和省部级项目，在线粒体氧化磷酸化功能改变与线粒体相关疾病、新冠病毒快速检测试剂方面取得突破，发表高水平论文百余篇。
+- **金大志研究员团队**：获省科技进步二等奖、三等奖各一项，省医药卫生科技进步一等奖一项、二等奖两项、三等奖一项，发表中科院一二区论文85篇，主编专业教材12部、主审7部。
+- **徐秀芳教授团队**：获国家自然科学基金3项、省部级项目20多项，获全国优秀教材二等奖一项。
+- **倪湘明教授团队**：获国家级课题23项、省级课题23项，省科技进步三等奖2项、省医药卫生科技进步二等奖2项，国家发明专利和实用新型专利77项，发表SCI论文150篇，主编专业书籍、主审教材8部、参编书籍40多部。
+- **李海教授团队**：主持参与国家级项目3项、省部级重点研发计划及200万以上重大项目，与中国人民解放军总医院、浙一医院、日本文化研究所等单位开展合作。
+- **阿尔茨海默病数字预警仪**：与浙大联合研制，已申报二类医疗器械，团队多次在医学人工智能大赛中获奖。
 ## 师资队伍与领军人物
-- **师资总体情况**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，其中正高35人、博士46人；专业背景涵盖临床检验诊断学、医学检验技术、影像技术、康复治疗学、智能医学工程、生化分子、免疫生物技术、微生物学、细胞生物学等。
-- **人才称号**：教育部医学技术类专业教学指导委员会委员1人，省万人创新人才2人次，浙江省151人才5人，省杰青1人，省高层次创新人才2人，省领军型创新创业团队1个。
-- **吕建新教授**：学位点负责人，博士，国家百千万人才工程入选者、国家行业专家、省万人计划领军人才；教育部医学技术类专业教学指导委员会委员、国家自然科学基金医学技术检验学科专家组组长、中华医学会检验学会教育学组组长；主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表高水平论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项。
-- **徐秀芳教授**：博士，浙江省151人才第三层次、省高校中青年学科带头人，现任研究生院院长兼医学影像学院院长，国家一流本科专业建设点（医学影像技术）负责人，教育部教指委相关医学分会委员、中华医学会影像技术分会委员；近三年以通讯作者或第一作者发表多篇高水平论文。
-- **叶祥明教授**：省人民医院主任医师、二级教授、博导、博士后导师，省康复中心主任、康复学院院长、省卫生领军人才、国家区域医疗中心浙江省重点培育专科康复医学学科带头人、数字化康复装备省部研究中心常务副主任；主持国家级课题3项、省重大课题2项，发表SCI论文98篇。
-- **金大志研究员**：博士、硕导，美国华盛顿大学博士后、美国MSCC访问学者，省创新人才、省卫生创新人才、省首届优秀医疗机器人才，现任检验医学院学术院长、省生物标志物与器官诊断转化重点实验室主任、中国医师协会临床微生物分会常务委员；主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划、省自然基金重点项目、省部共建重大项目共25项，发表SCI论文50多篇，参编专著6部，获省科技进步二等奖、三等奖各1项及美国微生物学年会重要奖项。
-- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士、早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长、智能医学工程学科负责人、浙江省中医药重点学科带头人，智慧健康装备领域专家；参与研制全生命周期中医治疗及康复医疗体系设备3台（套）。
+- **师资总体情况**：专任教师90人，高级职称53人（占30%以上），博士55人，专业背景涵盖临床检验诊断学、医学检验技术、影像技术、康复治疗学、智能医学工程、生化分子、免疫生物技术、微生物学、细胞生物学等。
+- **硕导队伍**：硕导69人，其中正高35人，博士46人。
+- **人才称号**：教育部医学技术类专业教学指导委员会委员、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省领军型创新创业团队1个。
+- **吕建新教授**：学位点负责人，博士，国家百千万人才工程、国家行业专家、省万人计划领军人才，教育部医学技术类专业教学指导委员会委员、国家自然基金会医学技术检验学科专家组长、中华医学会检验学会教育学组长，主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项。
+- **徐秀芳教授**：浙江省151人才第三层次、省高校中青年学科带头人，研究生院院长兼医学影像学院院长，国家一流本科专业建设点医学影像技术专业负责人，教育部教指委相关医学分会委员、中华医学会影像技术分会委员。
+- **叶祥明教授**：省人民医院主任医师、二级教授、博导、博士后导师，省卫生领军人才，国家区域医疗中心浙江省重点培育专科康复医学学科带头人，数字化康复装备省部研究中心常务副主任，主持国家级课题3项、省重大课题2项，发表SCI论文98篇。
+- **金大志研究员**：博士、硕导，美国华盛顿大学博士后、美国MSCC访问学者，省创新人才、省卫生创新人才，检验医学院学术院长、省生物标志物与器官诊断转化重点实验室主任，主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划等25项，发表SCI论文50多篇，获省科技进步二等奖、三等奖各一项。
+- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士、早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长、智能医学工程学科负责人、浙江省中医药重点学科带头人，研制全生命周期中医治疗及康复医疗体系设备3套。
 ## 硕士培养与毕业去向
-- **培养目标**：面向健康中国发展需要，紧密服务区域行业产业发展，围绕国际学术前沿、国际重大需求和转化研究，培养熟练掌握医学技术领域专业知识技能、具有良好创新实践能力的高层次应用型人才。
-- **培养方式与学制**：采用教学、专业实践与学位论文相结合方式；全日制专业学位学制三年，最长不超过五年。
-- **学分要求**：实行学分制，毕业前学业课程不少于24学分，其中专业必修课≥12学分（分方向），专业选修课≥6学分（可选智慧医疗、中医康复治疗学、生物信息学等）。
-- **培养环节**：第二学期开题，第三、四学期（研二）完成过程性考核，研二第二学期进行学位论文答辩。
-- **就业方向**：医院相关科室（检验方向可进检验科、输血科、病理科；影像方向可进放射科、超声科；康复方向可进康复医学科、骨科、神经科、运动医学科）、疾控中心（CDC，参与传染病防控、慢性病防治等公共卫生工作）、医药企业与生物技术公司（研发、生产、市场销售、质量管理与法规合规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）、药监局/卫健委/海关（医疗器械监管、卫生政策制定、口岸卫生检疫）、高校及研究所（读博深造或从事研究）。
-- **就业现状**：2025年开始招生，目前尚无毕业生。
+- **培养目标**：面向健康中国发展需要，紧密服务区域行业产业发展，培养熟练掌握医学技术领域专业知识技能、具有良好创新实践能力的高层次应用型人才。
+- **培养方式**：教学、专业实践与学位论文相结合。
+- **学制**：全日制专业学位学制三年，最长不超过五年。
+- **学分要求**：毕业前学业课程不少于24学分，其中专业必修课≥12学分（分方向），专业选修课≥6学分（含智慧医疗、中医康复治疗学、生物信息学等）。
+- **培养环节**：第二学期开题，第三、四学期过程性考核，研二进行学位论文答辩。
+- **医院就业方向**：检验方向可进入检验科、输血科、病理科；影像技术方向可进入放射科、超声科；康复治疗方向可进入康复医学科、骨科、神经科、运动医学科。
+- **公共卫生就业方向**：卫检方向可进入疾病预防控制中心（CDC），参与传染病防控、慢性病防治等公共卫生工作。
+- **企业就业方向**：医药企业与生物技术公司（研发、生产、市场销售、质量管理与法规合规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）。
+- **政府与事业单位就业方向**：药监局、卫健委、海关，从事医疗器械监管、卫生政策制定及口岸卫生检疫等工作。
+- **继续深造方向**：可到高校、研究所读博或从事研究工作。
+- **就业实例**：东阳市卫健委疾控中心招聘检验方向微生物检验、理化检验岗位，要求硕士及以上。
+- **毕业生情况**：2025年开始招生，目前尚无毕业生。
 ## 2026年招考计划
-- **计划招生**：2026年计划招生34人，仅供参考，以教育部正式下达人数为准。
-- **初试科目**：共三门，思想政治理论、英语为统考科目，专业课按方向自主命题：检验方向考检验综合、影像方向考医学影像技术综合、康复方向考康复治疗综合、智能医学工程方向考智能医学工程综合。
+- **计划招生人数**：2026年计划招生34人，实际以教育部2026年正式下达人数为准。
+- **初试科目**：思想政治理论、英语为统考科目，专业课按方向自主命题：检验考检验综合、影像技术考医学影像技术综合、康复治疗考康复治疗综合、智能医学工程考智能医学工程综合。
 - **检验综合考试内容**：分子生物学检验占40%、生物化学检验占30%、微生物学检验占30%。
-- **考试形式**：专业课满分300分，考试时长180分钟，考试大纲含考试内容、形式、试卷结构、知识点及参考书目，以杭州医学院研究生招生网公布为准。
-- **复试安排**：目前以线下为主，初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%，实行导师学生双向选择制。
-- **信息渠道**：杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）、杭州医学院研究生教育微信公众号。
+- **专业课考试形式**：满分300分，考试时长180分钟，考试大纲含考试内容、形式、试卷结构、知识点及参考书目。
+- **复试方式**：以线下为主，初试占60%、复试占40%。
+- **复试内容**：英语能力测试占20%、专业能力测试占40%、综合能力测试占40%，导师与考生采取双选制。
+- **信息发布渠道**：考试大纲及参考书目以杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）及杭州医学院研究生教育微信公众号公布为准。
 # 各方立场与诉求
-- **主持人**：代表后台考生提出就业前景关切，询问在当前经济形势下医学技术专业研究生毕业后的就业前景。
-- **宋宝峰**：回应称国家坚持就业优先，该专业就业面宽广、有竞争力，毕业生可继续深造读博，也可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等单位，研究生学历在杭州高水平三甲医院和企业中具有核心竞争力，呼吁考生不必过度担心和焦虑。
-- **主持人**：代考生询问硕士研究生入学考试初试科目有哪些，以便利用暑期备考。
-- **宋宝峰**：回应称初试共三门，思想政治理论和英语为统考，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合），并建议考生暑期重点备考，英语难度介于四级和六级之间，可参考研究生考试英语真题，同时关注杭州医学院研究生招生网和研究生教育微信公众号获取考试大纲与参考教材。
-- **主持人**：代考生询问跨专业报考的可能性，称有考生担心节奏快不起来。
-- **宋宝峰**：回应称医学技术专业鼓励跨学科跨专业报考，允许非本专业考生跨专业报考医学技术学位点，如从事检验方向可以跨专业自主报考，被录取概率会大大提高。
-- **主持人**：代考生询问学校交通条件和能否参加学科竞赛。
-- **宋宝峰**：回应称学校有三个校区，主校区在黄龙校区，位于主城区，交通便利；学校重视学科竞赛，研究生在竞赛中取得好成绩，有专门的选手讲座和培训，通过以赛促学、以赛促教、以赛促改提高教学质量和人才培养水平。
+- **宋宝峰（杭州医学院检验医学院、生物工程学院党委书记、副院长）**：面向考生及家长介绍医学技术专业硕士点情况，强调该学位点2024年获批、由5个学院共建、聚焦四个专业方向，并说明2025年已录取64位考生；回应考生对就业前景的关切，表示就业面宽广、有竞争力，对毕业生就业有信心。
+- **主持人**：代表后台考生提出关注问题，包括当前经济形势下研究生毕业后的就业前景、暑期如何备考初试科目、跨专业报考是否可行等；在节目最后请宋宝峰为考生送上祝福语。
+- **宋宝峰（回应就业前景问题）**：指出国家坚持就业优先，该专业培养高层次应用型医学技术人才，毕业生可继续深造读博，或进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等单位；杭州高水平三甲医院和企业对研究生及以上学位人才具有核心竞争力，考生不必过度担心和焦虑。
+- **宋宝峰（回应初试科目问题）**：说明初试共三门，思想政治理论和英语为统考，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；英语考试难度介于四级和六级之间，建议暑期作为备考关键期，关注学校研究生招生网和研究生教育微信公众号获取考试大纲与参考教材。
+- **宋宝峰（回应跨专业报考问题）**：明确表示允许并鼓励非本专业考生跨专业报考医学技术专业学位点，四个方向均可跨专业自主报考，跨专业考生被录取的概率会大大提高。
+- **宋宝峰（回应交通与竞赛问题）**：说明学校有三个校区，主校区在市中心黄龙校区，交通便利；学校重视学科竞赛，研究生在竞赛中取得好成绩，通过以赛促学、以赛促教、以赛促改提升教学质量与人才培养水平。
 # 达成共识
-- **学位点定位**：医学技术专业硕士点为2024年获批的新学位点，由检验医学院、生物工程学院（合署办公）牵头，医学影像学院、康复学院、信息工程学院共建，聚焦检验技术（医检、卫检）、医学影像技术、康复治疗、智能医学工程四个方向。
-- **2025年招生口径**：2025年录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
-- **2026年计划招生口径**：2026年计划招生34人，宋宝峰明确说明该数字仅供参考，**实际招生人数以教育部2026年正式下达人数为准**。
-- **初试科目口径**：初试共三门，思想政治理论、英语为统考科目，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）。
-- **复试安排口径**：复试目前以线下为主，初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%。
-- **跨专业报考口径**：宋宝峰明确表示**允许非本专业考生跨专业报考医学技术专业**，并称跨专业报考被录取的概率会大大提高。
-- **就业前景口径**：宋宝峰确认就业面宽广，包括深造读博、三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等方向，研究生学历具有核心竞争力。
-- **考试信息发布渠道**：宋宝峰确认考试大纲、参考书目等以杭州医学院研究生招生网及研究生教育微信公众号公布为准。
+- **学位点定位**：医学技术专业硕士点为2024年获批的新学位点，由检验医学院、生物工程学院（合署办公）牵头，医学影像学院、康复学院、信息工程学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个方向。
+- **招生口径**：2026年计划招生34人，宋宝峰明确说明**实际招生人数以教育部2026年正式下达人数为准**，计划数仅供参考。
+- **初试科目口径**：思想政治理论、英语为统考科目，专业课按方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合），考试大纲及参考书目以杭州医学院研究生招生网公布为准。
+- **复试口径**：复试以线下为主，初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%。
+- **跨专业报考口径**：宋宝峰明确表示**允许非本专业考生跨专业报考医学技术专业硕士点**，并鼓励跨学科跨专业考生报考。
+- **就业前景判断**：宋宝峰确认该专业就业面广泛，毕业生可进入医院相关科室、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校及研究所等，并称对毕业生就业**非常有信心**。
+- **培养目标确认**：培养面向健康中国发展需要、服务区域行业产业发展、具有创新实践能力的高层次应用型医学技术人才，采用教学、专业实践与学位论文相结合的培养方式。
 # 待协调事项与后续
 ## 待协调事项
-- **2026年计划招生人数**：目前公布为34人，仅供考生参考，实际招生人数以教育部2026年正式下达人数为准
-- **初试参考书及考试大纲**：以杭州医学院研究生招生网公布为准，直播中仅作初步介绍
+- **2026年实际招生人数**：以教育部正式下达人数为准，目前计划招生34人仅为参考
 - **复试具体形式与内容**：以学校复试录取办法为基础，目前可参考2025年复试办法
 ## 后续安排与参与方式
-- **直播回看**：本场直播结束后24小时内上传至B站，考生可随时搜索回看
-- **招生信息渠道**：持续关注杭州医学院官网及杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）
-- **微信公众号**：关注「杭州医学院研究生教育」微信公众号，可查看考试方向、考试大纲及参考教材书籍
-- **报考咨询**：考生可通过B站、微博、抖音弹幕区留言提问，直播中有嘉宾点评答疑
-- **学校地址**：杭州医学院有三个校区，主校区位于主城区黄龙校区，交通便利</t>
+- **直播回看**：本场直播结束后24小时内上传至B站，考生可随时搜索观看
+- **招生信息查询渠道**：杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn）、杭州医学院官网、杭州医学院研究生教育微信公众号
+- **考试大纲与参考书目**：以杭州医学院研究生招生网公布为准，含考试内容、考试形式、试卷结构及具体知识点
+- **初试科目**：思想政治理论、英语（统考），专业课按方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）
+- **复试安排**：以线下为主，初试占60%、复试占40%，复试含英语能力测试20%、专业能力测试40%、综合能力测试40%
+- **跨专业报考**：允许并鼓励非本专业考生跨专业报考医学技术专业硕士点
+- **校区情况**：学校有三个校区，主校区位于市中心黄龙校区，交通便利
+- **学科竞赛**：学校重视研究生学科竞赛，设有资源提升改善、专门讲座与培训，以赛促学、以赛促教、以赛促改</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>81.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23026/5854</t>
+          <t>23026/5902</t>
         </is>
       </c>
     </row>
@@ -11887,75 +11890,75 @@
       <c r="C32" t="inlineStr">
         <is>
           <t># 课程概况
-本次课程为历史小论文写作专题指导课，由老师主讲、学生参与互动。课程围绕小论文写作的核心要点展开，强调观点必须明确、论证一般写两到三条、结构需清晰（可按时间顺序或国内外等逻辑罗列）、结尾需升华观点，并指出写作前需审题、注意要求中的“小红帽”及形成标准，读材料需抓主要信息再细看关系，建议先写题目再罗列事实。课程依次讲解了自命题类、观点提示类和图表信息类题型的解题方法：自命题类需先审题明确要求，以武汉长江大桥为例说明背景部分需按时间顺序先写对内改革再写对外开放；观点提示类需选择核心观点并明确判断，不能照抄材料观点，需结合丝绸之路、四大发明等具体史实论述；图表信息类需快速看题头、横向纵向信息，注意信息之间的关系变化。课程通过例题分析进行实践指导，学生尝试分析各类题目，老师指出其问题并引导完善论述。
+本次课程为历史小论文写作专题课，围绕小论文的写作要求与各类题型的解题方法展开。老师首先强调小论文写作需观点明确、论证充分（一般写两到三条）、结构清晰（可按时间顺序或国内外等逻辑罗列），结尾需升华观点而非简单重复。随后系统讲解了自命题、观点提示、图表信息三类题型的解题步骤：自命题类需先审题（注意要求中的“小红帽”和形成标准），再读材料、抓主要信息、细看关系，先写题目再罗列与材料相关的事实；观点提示类需选择核心观点并明确表述，不能照抄材料；图表信息类需快速看题头、横向纵向信息，注意信息间关系变化并提取有效信息。例题分析环节，学生分析了武汉长江大桥材料（涉及新中国成立、改革开放背景）及观点提示类材料（含国民了解本国历史、敬畏祖国意志等四个观点），老师逐一指出作答中观点不明确、背景顺序不当等问题，并给出改进建议。
 # 核心知识点梳理
 ## 小论文写作基本要求
-- **观点明确**：写作必须亮出个人观点，不能只是“几个方面加个名词”的简单陈述，观点需有凝聚力。
-- **论证条数**：论证一般写**两到三条**，不宜过多；写一条难以支撑论点，太多则显冗长。
-- **结构清晰**：可按时间脉络（如先秦、明清时期）、国内外、内政外交等逻辑罗列，必须让阅卷者清楚看到分了几条。
-- **结尾升华**：最后论述需升华观点，不能简单把观点抄一遍；写作目的是升华观点，需简明有力。
-## 写作步骤与方法
-- **审题**：先阅读题目、慢点审题，注意要求中的“小红帽”及形成标准；如要求用世界史知识，就不能用中国史内容。
-- **读材料**：先大概看材料抓主要信息，再细看材料之间的关系，提取有效信息。
-- **列事实**：建议先写好题目，再罗列要用的史实，避免直接写在答题卡上出错后涂改；罗列的事实须与材料相关，不能乱列。
-- **论述顺序**：背景部分按时间顺序写，如“先写对内改革，再写对外开放”，不能颠倒。
-## 自命题类题型
-- **题型特点**：材料引出话题，需自行提炼观点并展开论述；以武汉长江大桥为例，可写“新中国成立”或“改革开放以来”背景。
-- **解题步骤**：审题看要求→读材料抓主要信息→先写题目→罗列相关史实→进行论述。
-- **易错点**：学生易只看到材料表面写得很好，却未明确自己的观点和背景；如写武汉长江大桥，需交代对内改革、对外开放的时间顺序。
-- **背景写法**：背景部分不能直接当成一个版本说，需按时间顺序展开，如先写对内改革再写对外开放。
+- **观点明确**：必须把观点亮出来，不能只是「几个方面加个名词」的简单陈述形式；观点需要凝聚、有针对性。
+- **论证条数**：论证一般写**两到三条**，不宜过多；写一条难以支撑论点，写太多则冗长。
+- **结构清晰**：可按时间脉络（如 700 时期、非常时期、明清时期）、国内外、内政外交等逻辑罗列，要让老师清楚看到写的是哪几条。
+- **结尾升华**：最后论述要升华观点，不能简单把观点抄一遍；写这个东西是为了升华观点。
+## 自命题类解题步骤
+- **审题**：先阅读题目、慢点审题，注意要求中的「小红帽」及形成标准；例如要求用世界史知识就不能搞成中国史模式。
+- **读材料**：认真读材料，先大概抓主要信息，再细看材料之间的关系。
+- **列事实**：先写好题目，再罗列要写的事实，事实须与材料相关，不要乱罗列；避免直接写在答题卡上导致写错又乱。
+- **写答案**：罗列清楚后再进行论述，最后升华观点。
+## 例题分析：武汉长江大桥
+- **学生作答**：发言人 2 提到武汉长江大桥与新中国成立、改革开放相关，认为材料体现「一个计划和一个减少」的转变。
+- **教师点评**：发言人 1 指出应先写对内改革、再写对外开放，按时间顺序排列；学生的问题在于未明确观点和背景顺序。
+- **写作要点**：可写「新中国成立刚刚成立」或「改革开放以来」作为背景，但必须写清楚具体时间和观点。
 ## 观点提示类题型
-- **题型特点**：材料给出若干观点，需选择核心观点并明确判断，如“我认为某观点是正确的/错误的”，不能照抄材料观点。
-- **材料示例**：以1940年抗战时期材料为例，包含四个观点——国民应略知本国历史、了解本国历史可维护国家利益、对本国历史有敬意则不会偏激理解、国民了解历史则国家才能发展。
-- **论述要求**：选择观点后需结合具体史实论证，如写“敬畏祖国意志”可引用丝绸之路、四大发明对欧洲的贡献、中华文化优越性等。
-- **易错点**：不能照抄材料观点，需有自己的表述；需注意材料写作的时代背景（如1940年抗战时期），说明为何此时提出该观点。
+- **解题方法**：先看材料中有哪些观点，再选择核心观点并明确表述；要表明「我认为什么观点是正确的或错误的」，不能照抄材料观点。
+- **例题材料**：材料含四个观点——①国民对其本国历史应略有所知；②了解本国历史会对国家利益产生威胁和利益；③对本国历史有悟空和定的时候不会偏激理解；④国民了解历史、反对偏激主义，国家才能继续发展。
+- **学生分析**：发言人 2 选择第二条观点，论证中华文化优越性（丝绸之路、四大发明对欧洲贡献、对东亚影响），并分析经济方面（新法探讨促进转化率）。
+- **教师点评**：发言人 1 指出学生未说明为什么在 1940 年抗战时期写这个东西，缺少时代背景分析；观点提示类题目需明确自己的观点，不能照抄材料。
 ## 图表信息类题型
-- **题型特点**：材料以图表、历史地图、建筑图片等形式呈现，需快速提取关键信息。
-- **解题步骤**：先看图表题头、横向纵向信息→注意信息之间的关系变化→提取有效信息→结合材料关系进行分析论述。
-- **历史地图题**：需在地图上画位置、判断地点，如涉及707年、1900年等时间点；注意地图与材料的对应关系。
-- **建筑类图表**：如展现两三个图线，需分析建筑与政治的关系，从建筑角度论述政治主题。
-- **图表关系题**：如涉及共同体、共同外交安全政策、司法和内部合作等大框架制度，需提取三个信息并分析其关系，再下结论。
-## 例题分析
-- **武汉长江大桥题**：学生分析时未明确观点和背景，老师指出应写新中国成立或改革开放背景，按时间顺序先写对内改革再写对外开放。
-- **观点提示材料题**：学生选择第二条观点（了解本国历史可维护国家利益），结合丝绸之路、四大发明对欧洲影响等史实论述，老师评价“写得还可以”。
-- **历史地图题**：涉及中国历代领导等级变化，学生写“古代人的变化与文学”，老师指出可结合儒家思想、社会状态分析各时期（春秋、东汉、宋明）等级变化原因。
-- **官方答案示例**：梁启超认为中国某时期具有合理性，突出“人人独善其身，人人相善其群”，用中华传统精神论证；唐朝国力强盛但民德较高，结论指向国家强盛、民德高尚与制度改善的关系。
+- **解题方法**：快速看图表关键信息（题头、横向纵向信息），注意信息之间的关系变化，提取有效信息再进行分析。
+- **例题特点**：图表信息类题目较难，涉及历史地图、数据变化等；需结合材料关系与所学知识进行论述。
+- **答题要求**：先找主要信息，不要逐点罗列；提出自己的看法，与「评析材料观点」有区别。
+## 易错点与注意事项
+- **观点表述**：不能只写一句诗作为观点，关键是合适；观点信息类必须表明观点。
+- **时代背景**：写历史小论文必须说明为什么在特定时期写这个东西，不能忽略时代背景。
+- **逻辑顺序**：按时间顺序写作时，应先写对内改革再写对外开放，不能颠倒。
+- **材料关系**：注意材料之间的相互关系，如共同体、共同外交安全政策、司法和内部合作等大框架制度内的小信息关系。
 # 课堂互动与答疑
-**学生**：小论文的论证部分一般写几条比较合适？写太多或太少会有什么问题？
-**教师**：论证一般写两到三条即可。写一条往往无法充分支撑论点，写太多则容易分散、难以深入。每条论证都要与材料相关，不能脱离材料乱罗列事实。
-**学生**：写小论文时，审题环节具体要注意什么？
-**教师**：审题要慢，先看题目要求，注意要求中是否有"小红帽"（即限定条件），以及评分标准。例如题目要求用世界史知识作答，就不能只写中国史内容；若限定了范围，也要严格遵循。审题不清是常见失分点。
-**学生**：观点提示类题目中，如何选择和处理材料给出的观点？
-**教师**：要在材料给出的多个观点中选择一个核心观点，明确表达自己认为该观点正确或错误，不能照抄材料原话。论述时需结合具体史实支撑自己的判断，并在结尾升华观点，不能简单重复开头。
-**学生**：图表信息类题目应该从哪些角度快速提取信息？
-**教师**：先看题头和横向、纵向栏目，抓住关键信息，再注意各信息之间的关系和变化趋势。例如历史地图要关注位置关系，数据表要关注数值变化。提取有效信息后再结合所学知识进行分析论述。
-**学生**：写作时是直接写在答题卡上，还是先打草稿？
-**教师**：建议先在草稿纸上写好题目，再罗列要使用的事实，确认逻辑清晰、与材料相关后再誊写到答题卡上，避免写错或涂改导致卷面混乱。
+**学生**：论证部分写几条比较合适？写一条行不行？
+**教师**：论证一般写两到三条，不宜过多。写一条难以支撑论点，写太多又显得冗长，两到三条最能有效支撑观点。
+**学生**：自命题类题目解题时，第一步应该做什么？
+**教师**：先审题，看清题目要求，注意要求中的“小红帽”和形成标准，明确题目限定的知识范围（如是否要求用世界史知识）。审题后再读材料，抓主要信息，细看材料之间的关系，最后先写题目、罗列与材料相关的事实，再写答案，避免直接写在答题卡上导致出错。
+**学生**：观点提示类题目和自命题类题目有什么区别？
+**教师**：观点提示类题目会给出若干观点，你需要选择其中一个核心观点并明确表述自己的判断（认为其正确或错误），不能照抄材料观点；自命题类则需自己提炼观点。前者重在评析材料观点，后者重在提出自己的看法。
+**学生**：图表信息类题目应该怎样快速提取信息？
+**教师**：先看题头和横向、纵向栏目，快速把握图表的关键信息，再注意各信息之间的关系变化，提取有效信息后结合材料进行分析，最后下结论。
+**学生**：写武汉长江大桥这道题时，背景部分按什么顺序写？
+**教师**：按时间顺序，先写对内改革，再写对外开放，不能颠倒顺序。同时要明确观点和背景，不能只罗列史实而不亮明自己的判断。
+**学生**：最后一段论述应该怎么写？
+**教师**：最后论述要升华观点，不能简单把观点再抄一遍。要结合论证内容进行总结提升，点明观点的意义或价值。
 # 课后任务与学习建议
 ## 课堂练习
-- **武汉长江大桥自命题练习**：考点为自命题类小论文审题与背景运用，需结合新中国成立或改革开放背景，按时间顺序先写对内改革再写对外开放，结论要点是明确观点并罗列与材料相关的事实。
-- **观点提示类材料练习**：考点为选择核心观点并明确判断，材料含四个观点（国民应了解本国历史、敬畏祖国意志、通达历史避免偏激、国家发展需历史认知），结论要点是结合丝绸之路、四大发明等史实论述，不能照抄材料观点。
-- **图表信息类练习**：考点为快速提取图表题头、横向纵向关键信息，注意信息间关系变化，结论要点是以历史地图、建筑与政治关系等为例，提取有效信息后进行分析论述。
-- **历史地图绘制练习**：考点为在地图上标注位置与关系，结论要点是注意地图信息与材料、实践的关系，再形成本文论述。
+- **武汉长江大桥自命题练习**：学生作答时提到新中国成立、改革开放等背景，老师指出应先写对内改革再写对外开放，且需明确观点与背景顺序，不能只罗列材料。
+- **观点提示类例题（钱穆《国史大纲》）**：材料含四个观点——国民应对本国历史略有所知、对本国历史应有温情与敬意、有历史知识者不会偏激理解或全盘否定古人、国家发展需国民具备历史认知。学生选第二条展开，从中华文化优越性、丝绸之路、四大发明对欧洲贡献等角度论证。
+- **图表信息类例题（历代民德变化）**：学生以「古代民德的变化与文学」为题，选取春秋、东汉、宋明等时期，分析民德高低与社会状态、制度的关系；老师提示可结合儒家思想地位变化、唐朝国力强盛但民德评价等角度。
+- **观点提示类例题（梁启超民德观）**：官方答案突出「人人独善其身，人人相善其群」，联系中华传统精神，并推论国家是否强盛、民德是否高尚与制度是否改善的关系。
 ## 复习重点
-- **观点明确**：小论文必须亮出明确观点，不能只是几个方面加名词的简单陈述，观点需有凝聚力。
-- **论证结构**：论证一般写两到三条，不宜过多，需按时间脉络（如先秦、明清时期）或国内外、内外等逻辑清晰罗列，让老师看清条理。
-- **结尾升华**：最后论述需升华观点，不能简单重复观点内容，要体现写作目的。
-- **审题要求**：注意题目要求中的"小红帽"及形成标准，如要求用世界史知识时不能搞错范围。
-- **材料阅读**：先大概看材料抓主要信息，再细看信息间关系，罗列事实需与材料相关，不能乱罗列。
+- **小论文写作要求**：观点必须明确亮出，不能只是简单陈述形式或几个方面加名词；论证一般写两到三条，太少无法支撑论点、太多则冗长。
+- **论证结构**：可按时间脉络（如先秦、明清）、国内外、内政外交等逻辑罗列，必须让老师清楚看到分了几条；最后论述要升华观点，不能简单把观点抄一遍。
+- **自命题类解题步骤**：先审题，注意要求中的「小红帽」和形成标准；再认真读材料、抓主要信息、细看材料间关系；先写题目，再罗列与材料相关的事实，最后写答案，避免直接写在答题卡上。
+- **观点提示类解题方法**：需选择核心观点并明确表述自己的判断（认为某观点正确或错误），不能照抄材料观点；论证时可用时间、国内外等角度展开。
+- **图表信息类解题方法**：快速看题头、横向纵向信息，注意信息之间的关系变化，提取有效信息后再进行分析。
 ## 学习建议
-- **先写题目再作答**：写作前先把题目写好，再罗列要写的事实，避免直接在答题卡上写导致出错或混乱。
-- **观点提示类选核心观点**：需在多个观点中选择一个核心观点，明确判断其正确或错误，并在论点中详细表述，不能照抄材料。
-- **图表类快速抓关键**：迅速看图表题头、横向纵向信息，注意信息间关系变化，提取有效信息后再分析。
-- **结合史实论述**：论述需结合具体史实支撑观点，如丝绸之路、四大发明对欧洲的贡献等，不能只写空泛结论。</t>
+- **审题放慢**：老师强调「要慢点审题」，看清题目要求（如是否限定用世界史知识、是否限定范围），注意要求中的「小红帽」和形成标准。
+- **先打草稿再誊写**：题目先写好，再罗列要写的事实，确认与材料相关后再写答案，避免在答题卡上写错又乱。
+- **论证条数控制**：论证写两到三条即可，不要写一条也不要写太多，确保每条都能支撑论点。
+- **结合时代背景分析**：写历史小论文时需思考「为什么在这个时期写这个东西」，如钱穆1940年抗战时期写《国史大纲》的目的，不能只罗列史实。
+- **观点要明确表态**：观点提示类题目必须形成自己的观点，不能只是简单复述材料，可用「我认为……」「我不同意他的观点」等句式明确立场。</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12357/3382</t>
+          <t>12357/3459</t>
         </is>
       </c>
     </row>
@@ -12112,139 +12115,164 @@
       <c r="C33" t="inlineStr">
         <is>
           <t># 报告概况
-十四届全国人大三次会议于2025年开幕，出席代表2929人，当日出席2880人、缺席49人，出席人数符合法定人数，会议第一项议程为审议政府工作报告，由国务院总理李强代表国务院作报告。报告回顾2024年工作，指出面对外部压力加大、内部困难增多的复杂严峻形势，全年经济社会发展主要目标任务顺利完成，国内生产总值达134.9万亿元、增长5%，城镇新增就业1256万人，居民消费价格上涨0.2%，粮食产量首次跃上1.4万亿斤，新能源汽车年产量突破1300万辆，嫦娥六号实现人类首次月球背面采样返回；同时坦承内需不振、预期偏弱等问题交织叠加。报告提出2025年经济社会发展总体要求与主要预期目标，部署大力提振消费、因地制宜发展新质生产力、深入实施科教兴国战略、推动标志性改革举措加快落地、扩大高水平对外开放、有效防范化解重点领域风险、着力抓好三农工作、协同推进降碳减污扩绿增长、加大保障和改善民生力度、维护国家安全和社会稳定等十大任务，整体基调为坚持稳中求进、迎难而上，高质量完成“十四五”规划目标任务。
+十四届全国人大三次会议于2025年开幕，出席代表2929人，今日出席2880人、缺席49人，出席人数符合法定人数，会议第一项议程为审议政府工作报告，由国务院总理李强代表国务院作报告。报告回顾2024年工作：国内生产总值达134.9万亿元、增长5%，城镇新增就业1256万人，城镇调查失业率平均5.1%，居民消费价格上涨0.2%，外汇储备超3.2万亿美元，粮食产量首次跃上1.4万亿斤，新能源汽车年产量突破1300万辆，嫦娥六号实现人类首次月球背面采样返回，全年经济社会发展主要目标任务顺利完成。报告提出2025年主要预期目标为国内生产总值增长5%左右、城镇调查失业率5.5%左右、城镇新增就业1200万人以上、居民消费价格涨幅2%左右、粮食产量1.4万亿斤左右、单位国内生产总值能耗降低3%左右，并部署大力提振消费、因地制宜发展新质生产力、深入实施科教兴国战略、推动标志性改革举措加快落地、扩大高水平对外开放、有效防范化解重点领域风险、着力抓好三农工作、协同推进降碳减污扩绿增长、加大保障和改善民生力度、维护国家安全和社会稳定等十大方面政府工作任务，整体基调为坚持稳中求进、迎难而上，高质量完成“十四五”规划目标任务。
 # 核心政策
-## 核心政策
-### 2025年经济社会发展主要预期目标
-- **国内生产总值增长5%左右**，既是稳就业、防风险、惠民生的需要，也有经济增长潜力和有利条件支撑，并与中长期发展目标相衔接
-- **城镇调查失业率5.5%左右**，**城镇新增就业1200万人以上**
-- **居民消费价格涨幅2%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡
-- **粮食产量1.4万亿斤左右**，**单位国内生产总值能耗降低3%左右**，生态环境质量持续改善
-### 宏观政策取向
-- **财政政策**：今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；拟发行超长期特别国债**1.3万亿元**，更大力度支持`两重`建设；拟发行特别国债**5000亿元**支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**
-- **货币政策**：实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配
+## 2025年经济社会发展主要预期目标
+- **国内生产总值**：增长**5%左右**，既是稳就业、防风险、惠民生的需要，也有经济增长潜力和有利条件支撑，并与中长期发展目标相衔接
+- **就业**：城镇调查失业率**5.5%左右**，城镇新增就业**1200万人以上**
+- **物价**：居民消费价格涨幅**2%左右**
+- **居民收入**：居民收入增长和经济增长同步
+- **国际收支**：保持基本平衡
+- **粮食产量**：**1.4万亿斤左右**
+- **能耗与生态**：单位国内生产总值能耗降低**3%左右**，生态环境质量持续改善
+## 财政政策
+- **赤字安排**：今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**
+- **超长期特别国债**：拟发行**1.3万亿元**，其中**3000亿元**支持消费品以旧换新，更大力度支持`两重建设`
+- **特别国债**：拟发行**5000亿元**，支持国有大型商业银行补充资本
+- **地方政府专项债券**：安排**4.4万亿元**
+- **债务总规模**：今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**
+- **支出导向**：中央财政加大地方一般性转移支付力度，筑牢兜实基层`三保`底线；政府坚持过紧日子，腾出更多资金用于发展所需、民生所需
+## 货币政策
+- **基调**：实施适度宽松的货币政策，适时降准降息，保持流动性充裕
+- **目标匹配**：使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配
+- **工具创新**：优化和创新结构性货币政策工具，更大力度促进楼市股市健康发展
+- **传导机制**：进一步疏通货币政策传导渠道，推动社会综合融资成本下降
+## 宏观政策导向
 - **民生导向**：强化宏观政策民生导向，经济政策的着力点更多转向惠民生、促消费，推动更多资金资源投资于人、服务于民生
-- **政策协同**：健全和用好宏观政策取向一致性评估工作机制，提升政策目标、工具、时机、力度、节奏的匹配度，注意倾听市场声音
-### 扩大内需与产业发展政策
-- 实施`提振消费专项行动`，制定提升消费能力、增加优质供给、改善消费环境专项措施；安排超长期特别国债**3000亿元**支持消费品以旧换新
-- 扩大有效投资：今年中央预算内投资已安排**7350亿元**；优化地方政府专项债券管理机制，支持和鼓励民间投资发展
-- 培育壮大新兴产业、未来产业：开展`新技术、新产品、新场景大规模应用示范行动`，培育生物制造、量子科技、具身智能、6G等未来产业
-- 推动传统产业改造升级：深入实施`制造业重大技术改造升级和大规模设备更新工程`，加快制造业数字化转型
-- 激发数字经济创新活力：持续推进`人工智能+`行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用
-### 科教兴国与改革开放政策
-- 加快建设高质量教育体系：制定实施`教育强国建设三年行动计划`，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，**逐步推行免费学前教育**
-- 推进高水平科技自立自强：加快组织实施和超前布局重大科技项目，加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目
-- 推动标志性改革举措落地：高质量完成`国有企业改革深化提升行动`，开展`规范涉企执法专项行动`，纵深推进全国统一大市场建设，综合整治`内卷式竞争`，修订出台新版市场准入负面清单
-- 深化财税金融体制改革：开展中央部门`零基预算改革试点`，加快推进部分品目消费税征收环节后移并下划地方，大力推动中长期资金入市
-- 扩大高水平对外开放：扩大电信、医疗、教育等领域开放试点，推动高质量共建`一带一路`走深走实，持续扩大面向全球的高标准自由贸易区网络
-### 风险防范与民生保障政策
-- 推动房地产市场止跌回稳：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，加快构建房地产发展新模式
-- 稳妥化解地方政府债务风险：完善和落实`一揽子化债方案`，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，坚决遏制违规举债行为
-- 积极防范金融领域风险：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险
-- 稳定和扩大就业：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，开展大规模职业技能提升培训
-- 强化基本医疗卫生服务：深化以公益性为导向的公立医院改革，优化药品集采政策，严格医保基金监管
-- 完善社会保障：**城乡居民基本养老金最低标准再提高20元**，适当提高退休人员基本养老金；制定促进生育政策，**发放育儿补贴**，大力发展托幼一体服务
-### 绿色转型与三农政策
-- 协同推进降碳、减污、扩绿、增长：持续深入推进蓝天碧水净土保卫战，全面推进以国家公园为主体的自然保护地体系建设
-- 积极稳妥推进碳达峰碳中和：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度，加快建设沙戈荒新能源基地，开展煤电低碳化改造试点示范
-- 增强粮食等重要农产品稳产保供能力：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`
-- 巩固拓展脱贫攻坚成果：提高监测帮扶效率，确保不发生规模性返贫致贫，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度
-- 推进农村改革发展：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围
+- **政策组合拳**：健全和用好宏观政策取向一致性评估工作机制，提升政策目标、工具、时机、力度、节奏的匹配度
+- **预期引导**：注意倾听市场声音，协同推进政策实施和预期引导
+## 扩大内需政策
+- **提振消费**：实施`提振消费专项行动`，制定提升消费能力、增加优质供给、改善消费环境专项措施
+- **以旧换新**：安排超长期特别国债**3000亿元**支持消费品以旧换新
+- **服务消费**：扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力
+- **有效投资**：今年中央预算内投资已安排**7350亿元**，用好超长期特别国债更大力度支持`两重建设`
+- **民间投资**：优化地方政府专项债券管理机制，支持和鼓励民间投资发展
+## 产业与创新政策
+- **新兴产业**：深入推进战略性新兴产业融合集群发展，开展`新技术、新产品、新场景大规模应用示范行动`
+- **未来产业**：培育生物制造、量子科技、具身智能、6G等未来产业
+- **传统产业**：深入实施`制造业重大技术改造升级和大规模设备更新工程`，开展`标准提升引领传统产业优化升级行动`
+- **数字经济**：持续推进`人工智能+`行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用，优化全国算力资源布局
+- **科技自立自强**：加快组织实施和超前布局重大科技项目，加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目
+## 教育人才政策
+- **教育强国**：制定实施`教育强国建设三年行动计划`，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育
+- **高等教育**：扎实推进优质本科扩容，加快`双一流`建设
+- **人才队伍**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，深化人才分类评价改革
+## 改革开放政策
+- **国企改革**：高质量完成`国有企业改革深化提升行动`
+- **民营经济**：扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展`规范涉企执法专项行动`
+- **统一大市场**：纵深推进全国统一大市场建设，破除地方保护和市场分割，综合整治`内卷式竞争`，修订出台新版市场准入负面清单
+- **财税改革**：开展中央部门`零基预算改革试点`，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方
+- **资本市场**：深化资本市场投融资综合改革，大力推动中长期资金入市
+- **对外开放**：扩大电信、医疗、教育等领域开放试点，推动高质量共建`一带一路`走深走实，持续扩大面向全球的高标准自由贸易区网络
+## 风险防范政策
+- **房地产**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，推动建设安全、舒适、绿色、智慧的好房子
+- **地方债务**：完善和落实一揽子化债方案，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，坚决遏制违规举债行为
+- **金融风险**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险，健全金融监管体系，强化央地监管协同
+## 三农与区域政策
+- **粮食安全**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`
+- **巩固脱贫**：提高监测帮扶效率，确保不发生规模性返贫致贫，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度
+- **农村改革**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围
+- **新型城镇化**：深入实施`新型城镇化战略行动`，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务，持续推进城市更新和城镇老旧小区改造
+- **区域战略**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，支持经济大省挑大梁
+## 绿色转型政策
+- **污染防治**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程
+- **低碳经济**：深入实施`绿色低碳先进技术示范工程`，培育绿色建筑等新增长点，加强废弃物循环利用，健全绿色消费激励机制
+- **双碳目标**：积极稳妥推进碳达峰碳中和，建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度，加快建设沙戈荒新能源基地，开展煤电低碳化改造试点示范
+## 民生保障政策
+- **就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，开展大规模职业技能提升培训行动
+- **医疗**：深化以公益性为导向的公立医院改革，实施`医疗卫生强基工程`，优化药品集采政策，健全药品价格形成机制，支持创新药发展，严格医保基金监管
+- **养老**：城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金，推进社区支持的居家养老，强化失能老年人照护
+- **生育**：制定促进生育政策，发放育儿补贴，大力发展托幼一体服务
+- **社会救助**：完善分层分类社会救助体系，保障困难群众基本生活
+- **安全治理**：深入实施`安全生产治本攻坚三年行动`，抓好校园学生餐、平台外卖安全监管，推进基层综治中心规范化建设
 # 重点工作
 ## 大力提振消费、提高投资效益，全方位扩大国内需求
 - **提振消费专项行动**：制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力，多渠道促进居民增收
 - **消费品以旧换新**：安排超长期特别国债3000亿元支持消费品以旧换新
 - **扩大服务消费**：扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力
-- **消费者权益保护**：强化消费者权益保护，营造安心放心消费环境
+- **强化消费者权益保护**：营造安心放心消费环境
 - **扩大有效投资**：发挥好各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目，管好用好资金，坚决防止低效无效投资
-- **投资安排**：今年中央预算内投资已安排7350亿元；用超长期特别国债更大力度支持"两重"建设
+- **投资规模安排**：今年中央预算内投资已安排7350亿元；用超长期特别国债更大力度支持"两重"建设
 - **民间投资**：优化地方政府专项债券管理机制，支持和鼓励民间投资发展，让民间资本有更大发展空间
 ## 因地制宜发展新质生产力，加快建设现代化产业体系
-- **培育新兴产业、未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动
+- **培育壮大新兴产业、未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动
 - **未来产业布局**：培育生物制造、量子科技、具身智能、6G等未来产业
-- **产业统筹与创新企业培育**：加强产业统筹布局和产能监测预警，梯度培育创新型企业，让更多企业在新领域新赛道跑出加速度
+- **产业统筹与创新型企业培育**：加强产业统筹布局和产能监测预警，梯度培育创新型企业，让更多企业在新领域新赛道跑出加速度
 - **传统产业改造升级**：深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型，开展标准提升引领传统产业优化升级行动，打造名品精品经典产业
-- **数字经济创新**：持续推进"人工智能+"行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端
+- **激发数字经济创新活力**：持续推进"人工智能+"行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端
 - **数字基础设施**：扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展
 ## 深入实施科教兴国战略，提升国家创新体系整体效能
 - **高质量教育体系建设**：制定实施教育强国建设三年行动计划，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育
-- **高等教育与教师队伍**：扎实推进优质本科，加快"双一流"建设；建设高素质专业化教师队伍，加强师德师风建设
-- **科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革
-- **产学研融合**：加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目
-- **科技成果转化**：健全科技成果转化支持政策和市场服务，加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境
+- **高等教育与教师队伍**：扎实推进优质本科，加快"双一流"建设，建设高素质专业化教师队伍，加强师德师风建设
+- **推进高水平科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革
+- **产学研深度融合**：加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目
+- **科技成果转化与创新环境**：健全科技成果转化支持政策和市场服务，加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境
 - **人才队伍建设**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革
 ## 推动标志性改革举措加快落地，更好发挥经济体制改革牵引作用
-- **国有企业改革**：高质量完成国有企业改革深化提升行动
-- **民营经济发展**：扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动
+- **激发经营主体活力**：坚持和落实"两个毫不动摇"，高质量完成国有企业改革深化提升行动，扎实落实促进民营经济发展的政策措施
+- **涉企服务与清欠**：加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动
+&gt; 政府要寓管理于服务之中，用服务的暖心增强企业的信心。
 - **全国统一大市场建设**：破除地方保护和市场分割，综合整治"内卷式"竞争，修订出台新版市场准入负面清单，优化新业态新领域市场准入环境
-- **信用与退出机制**：构建统一的信用修复制度，完善企业简易注销，逐步推广新主体活动发生地统计
-- **财税体制改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方
+- **制度性改革**：构建统一的信用修复制度，完善企业简易注销，逐步推广经营主体活动发生地统计
+- **财税金融体制改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方
 - **资本市场改革**：深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设
 ## 扩大高水平对外开放，积极稳外贸、稳外资
-- **稳定对外贸易**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设
-- **外贸新增长点**：拓展境外经贸合作区功能，支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点
-- **吸引外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，加强外资企业服务保障
+- **稳定对外贸易发展**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设
+- **拓展外贸新空间**：拓展境外经贸合作区功能，支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点
+- **大力鼓励外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，加强外资企业服务保障
 - **自贸试验区建设**：推动自贸试验区提质增效和扩大改革任务授权，持续营造市场化、法治化、国际化一流营商环境
 - **共建"一带一路"**：统筹推进重大标志性工程和"小而美"民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局
 - **多双边和区域经济合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制
 ## 有效防范化解重点领域风险，牢牢守住不发生系统性风险底线
-- **房地产市场止跌回稳**：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，有序搭建相关制度
-- **房地产发展新模式**：加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子
-- **地方政府债务风险化解**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作
-- **政府债务管理**：完善政府债务管理机制，坚决遏制违规举债行为
-- **金融领域风险防范**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险
-- **金融监管体系**：健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案，有效维护金融安全稳定
+- **推动房地产市场止跌回稳**：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险
+- **构建房地产发展新模式**：有序搭建相关基础性制度，推动建设安全、舒适、绿色、智慧的好房子
+- **稳妥化解地方政府债务风险**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作
+- **完善政府债务管理机制**：坚决遏制违规举债行为
+- **积极防范金融领域风险**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险
+- **健全金融监管体系**：强化央地监管协同，完善应对外部风险冲击预案，有效维护金融安全稳定
 ## 着力抓好"三农"工作，深入推进乡村全面振兴
-- **粮食稳产保供**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设
-- **种业振兴与农机装备**：深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广
+- **增强粮食等重要农产品稳产保供能力**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设
+- **种业振兴与农业科技推广**：深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广
+&gt; 各地区都要扛稳保障国家粮食安全责任，共同把饭碗端得更牢。
 - **巩固拓展脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫，加强易地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度
-- **帮扶制度完善**：统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系
-- **农村改革发展**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围
-- **兴业强县富民**：因地制宜推动兴业强县富民一体发展，拓宽农民增收渠道，持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村
+- **完善帮扶制度体系**：统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系
+- **扎实推进农村改革发展**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围
+- **促进县域经济发展与农民增收**：因地制宜推动兴业、强县、富民一体发展，拓宽农民增收渠道，持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村
 ## 推进新型城镇化和区域协调发展，进一步优化发展空间格局
-- **农业转移人口市民化**：科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务
-- **随迁子女与住房保障**：强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道
-- **城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市
-- **区域战略实施**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极
-- **区域产业协作**：支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东中西、东北地区产业协作
+- **深入实施新型城镇化战略行动**：科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务
+- **农业转移人口保障**：强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道
+- **城市更新与老旧小区改造**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市
+- **加大区域战略实施力度**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极
+- **区域产业协作**：支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东、中、西、东北地区产业协作
 ## 协同推进降碳、减污、扩绿、增长，加快经济社会发展全面绿色转型
-- **污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程
+- **加强污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程
 - **美丽中国先行区建设**：积极推进美丽中国先行区建设，不断满足人民群众对良好生态环境的新期待
-- **绿色低碳经济**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用
-- **绿色消费机制**：健全绿色消费激励机制，推动形成绿色低碳生产方式和生活方式
-- **碳达峰碳中和**：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度
-- **能源与气候治理**：加快建设沙戈荒新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理
+- **加快发展绿色低碳经济**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用
+- **健全绿色消费激励机制**：推动形成绿色低碳生产方式和生活方式
+- **积极稳妥推进碳达峰碳中和**：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度
+- **能源与气候治理**：加快建设"沙戈荒"新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理
 ## 加大保障和改善民生力度，提升社会治理效能
-- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换
-- **就业创业服务**：优化就业创业服务，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障
-- **职业技能培训**：开展大规模职业技能提升培训行动，让多劳者多得、技高者多得、创新者多得
-- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程
-- **药品集采与医保监管**：优化药品集采政策，强化质量评估和监管；健全药品价格形成机制，支持创新药发展；完善中医药传承创新发展机制；严格医保基金监管，让每一分钱都用于增进人民健康福祉
-- **社会保障**：城乡居民基础养老金最低标准再提高20元，适当提高退休人员基本养老金
-- **养老服务**：推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、辅助器具购置和租赁支持力度
-- **生育支持**：制定促进生育政策，发放育儿补贴，大力发展托幼一体服务
-- **社会救助**：完善分层分类社会救助体系，保障困难群众基本生活
-- **精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业，推动优质文化资源直达基层
-- **全民健身**：推进群众身边的运动场地设施建设，广泛开展全民健身活动，加强青少年科学健身和健康干预
-- **国家安全和社会稳定**：全面贯彻总体国家安全观，深入实施安全生产治本攻坚三年行动，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对
-- **基层治理与法律服务**：推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国
-## 政府自身建设与国防外交
-- **"十五五"规划编制**：今年将开展"十五五"规划编制工作，科学确定发展目标，谋划好重大战略任务、重大政策举措、重大工程项目
-- **法治政府建设**：严格依照宪法法律履职尽责，自觉接受同级人大及其常委会监督、人民政协民主监督、社会和舆论监督，加强审计监督
-- **行政效能提升**：把面向基层的督查检查考核减下来，让广大干部把更多时间和精力用到干实事上
-- **民族团结与宗教侨务**：以铸牢中华民族共同体意识为主线，推进民族团结进步事业；坚持党的宗教工作基本方针，积极推进我国宗教中国化；完善侨务工作机制
-- **国防和军队建设**：贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全力打好实现建军一百年奋斗目标攻坚战，深入推进练兵备战，协力推进跨军地改革
-- **港澳工作**：全面准确、坚定不移贯彻"一国两制"、"港人治港"、"澳人治澳"、高度自治的方针，落实爱国者治港、爱国者治澳原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局
-- **对台工作**：坚持一个中国原则和"九二共识"，坚决反对"台独"分裂和外部势力干涉，推动两岸关系和平发展，完善促进两岸经济文化交流合作机制和政策
-- **外交工作**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，推动落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体</t>
+- **更大力度稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换
+- **就业创业服务**：拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障，开展大规模职业技能提升培训行动
+&gt; 让多劳者多得，技高者多得，创新者多得。
+- **强化基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程，优化药品集采政策，强化质量评估和监管
+- **药品与中医药发展**：健全药品价格形成机制，支持创新药发展，完善中医药传承创新发展机制，加强疾病预防控制体系建设
+- **严格医保基金监管**：让每一分钱都用于增进人民健康福祉
+- **完善社会保障和服务政策**：城乡居民基础养老金最低标准再提高20元，适当提高退休人员基本养老金
+- **养老与生育支持**：推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、康复辅助器具购置和租赁支持力度；制定促进生育政策，发放育儿补贴，大力发展托幼一体服务
+- **完善社会救助体系**：完善分层分类社会救助体系，保障困难群众基本生活
+- **加强精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业，推动优质文化资源直达基层
+- **全民健身与青少年健康**：推进群众身边的运动场地设施建设，广泛开展全民健身活动，加强青少年科学健身和健康干预
+- **维护国家安全和社会稳定**：全面贯彻总体国家安全观，加强公共安全治理，深入实施安全生产治本攻坚三年行动
+- **重点领域安全监管**：抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对，推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10273/7336</t>
+          <t>10273/8020</t>
         </is>
       </c>
     </row>
@@ -12457,53 +12485,56 @@
       <c r="C34" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为景城苑小区物业招标答疑会，业主代表就改造计划、停车管理、承接查验、安防停车、杂物晾晒等问题向两家投标物业公司（富家物业、知名管理）提问，两家公司分别作答。富家物业预计改造在一年内完成，针对停车乱象先分析原因再制定措施，承接查验提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先与现物业私下沟通，必要时在业委会或街道社区许可下采取强制措施；安防改善包括增设人行门禁、升级大堂报到系统、增设隔离墩、建设外围停车场并安装停车管理系统、增设电动车停车场。知名管理成立于2004年，总部在深圳，全国367个项目、127个业委会项目；团队编制16人，薪酬福利高于周边同类项目，一线人员不外包；进场第一个月集中资源进行环境绿化清洁整改，半年内排查设备设施，八个月内保证项目有效运作；包干制下保证财务透明，每季度公示物业管理费和停车费；承接查验前与社区街道派出所沟通，与现物业和业委会明确设备设施和债务债权，增派150%人员；安防措施包括关键岗位用老员工、收集业主车辆信息、制定停车管理方案、升级门禁系统；针对楼层杂物采取宣传引导、联合社区、沟通限期处理、提供临时堆放区，强调疏导而非强制；针对晾晒问题计划设置集中晾晒区，提供免费上门晾晒服务。评标委员会打分后，主持人宣布各公司得分：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源新东源物业管理有限公司54.48分，中标候选人为深圳市资平物业发展有限公司。打分环节全程保密，暂停网络直播，录像材料不予公开；总评委打分去掉一个最高分和最低分。
+景城苑小区召开物业招标答疑会，由业委会组织，两家物业公司（长沙富佳物业管理有限公司、深圳市资平物业发展有限公司）分别应答业主提问，评标委员会随后打分并公布结果。会议围绕改造计划与时间、承接查验与交接、安防与停车管理、业主满意度与收费率、包干制经验与公益服务、楼层杂物与晾晒问题等板块展开。最终深圳市资平物业发展有限公司以第一名中标，长沙富佳物业管理有限公司以72.91分位列第二，湖南恒居恒基居业物业管理有限公司60.73分列第三，重庆新东源新东源物业管理有限公司54.48分列第四。两家公司均承诺一年内完成主要改造；资平物业计划进场第一个月集中整治环境绿化，半年内处理设备设施，八个月内完成主要改造。评标打分去掉一个最高分和最低分，打分环节全程保密，暂停网络直播，录像材料不予公开。
 # 分段速览
-## 00:00:10-00:09:25 富家物业答疑
-业主代表首先提问富家物业若中标后从哪些方面改善小区现状及预计时间，发言人1回应称具体改造项目已在标书117页详细说明，预计改造时间在一年内完成。随后业主代表反映考察中发现卫生室存在车辆停放不规范、电动车乱停现象，发言人1表示应先分析乱停原因，若是停车位不够则增加停车位，若是业主不自觉则派保安、客服人员现场说服劝阻纠正。第三个问题关于承接查验工作，发言人1介绍富家物业有丰富二手小区交接经验，提前两周项目负责人入场摸底，提前一周服务人员到位培训，交接不畅时先与现物业私下沟通，无法解决则请业委会或街道社区组织协调会，仍无法解决则在获得许可下采取强制措施。第四个问题涉及监控门禁失效导致人员车辆随意进出及停车混乱，发言人1提出五项措施：大门口增设人行门禁系统、升级大堂报到系统、增设隔离墩、建设外围停车场并安装停车管理系统、增设电动车停车场。最后一个问题关于类似项目管理经验及满意度与收费率措施，发言人1表示没有与景城苑很相似的小区，处理问题采用四句话：用心倾听、如实记录、马上处理、及时反馈。
-## 00:09:36-00:12:22 评标流程说明
-业主代表宣布深圳市资平物业发展有限公司代表上场，并说明抢标时间为10分钟，每道题答题时间为3分钟。评标流程为各投标公司依次答辩后由评标委员会打分。
-## 00:12:22-00:19:44 知名管理公司介绍与答疑
-知名管理发言人介绍公司成立于2004年，总部在深圳，是全国市场化物业公司，无开发背景，目前全国有367个项目，其中127个为业委会项目。公司创始人陈志平先生原为万科物业创始人，曾协同建立中国第一个业委会。公司为中国物业管理协会副会长单位、全国百强企业。针对景城苑项目，公司打造"让一线权利归还业主"理念，确保财务透明和管理透明，包干制下每季度公示物业管理费和停车费。团队编制16人，薪酬福利高于周边同类项目，一线人员不外包。进场第一个月调动湖南战队其他项目资源进行环境绿化清洁全面清扫，半年内调动集团设备公司工程师对设备设施全面排查诊断，八个月内保证项目有效运作。公司导入顾客管理系统集中处理业主投诉咨询报事，形成大数据库管理业主咨询投诉，并针对老龄化开展社区文化活动，每两个月开展一次。
-## 00:19:52-00:34:44 知名管理答疑
-业主代表提问若知名管理中标后如何改造小区及预计时间，发言人回应经查勘主要存在安全管控、设备设施维护、环境、社区氛围四方面问题，进场第一个月集中资源整改环境绿化，半年内排查设备设施，八个月内达到有序状态，一年内保证小区整体有序。第二个问题关于包干制经验及公益性拓展服务，发言人介绍公司在长沙有11个项目，其中10个为包干制，强调包干制下保证业主知情权、增加与业委会互动、团队直招，管理干部30%来自现有团队、60%左右来自现有物业优秀员工或重新招聘；公益性服务包括居家上门免费服务、家政、24小时业主护送服务等。第三个问题关于承接查验，发言人表示前期准备要充足，与社区街道派出所沟通，与现物业和业委会明确设备设施和债务债权，按专业线分专业组查验，调动集团工程师协助，增派150%人员。第四个问题关于安防停车，发言人提出关键岗位用老员工保证责任心，收集业主车辆信息制定停车管理方案，升级门禁系统识别外来人员，通过技术手段梳理把控监控。第五个问题关于楼层顶层堆放杂物和乱搭乱晒，发言人强调宣传引导、联合社区应急管理部门、上门沟通限期处理、提供临时堆放区，强调疏导而非强制；针对晾晒问题计划设置集中晾晒区，提供免费上门晾晒服务。
+## 00:00:10-00:09:36 富佳物业答疑
+业主代表就小区管理问题向富佳物业提问，富佳物业发言人逐一回应。关于改造计划，富佳物业表示具体改造项目已在标书117页详细说明，预计一年内完成系列改造。针对卫生室及小区车辆乱停问题，富佳物业提出先分析原因，若停车位不够则增加车位，若业主不自觉则由保安和客服人员现场说服劝阻纠正。关于与原物业的承接查验，富佳物业介绍其接手二手小区经验丰富，提前两周入场摸底、提前一周安排服务人员培训，交接不畅时先与原物业私下沟通，解决不了则请业委会或街道社区组织协调会，仍无法解决时在获得业委会、业主大会及街道社区许可下采取强制措施。针对监控门禁失效和停车混乱，富佳物业提出增设人行门禁系统、升级大堂报到系统、增设隔离墩、建设外围停车场并安装停车管理系统、增设电动车停车场等五项措施。关于业主满意度和收费率，富佳物业提出“用心倾听、如实记录、马上处理、及时反馈”的四句话方法。
+## 00:10:00-00:19:44 资平物业介绍
+富佳物业答疑结束后，深圳市资平物业发展有限公司代表上台介绍公司情况。资平物业成立于2004年，总部在深圳，为全市场化物业公司，无开发背景，目前在全国有367个项目，其中127个为业委会项目。公司创始人陈志平先生原为万科物业创始人，曾协同建立中国第一个业委会。资平物业现为中国物业管理协会副会长单位及全国百强企业。针对景城苑项目，资平物业提出“让一线权利归还业主”的理念，确保财务透明和管理透明，每季度公示物业管理费和停车费，邀请业主参与公共事务管理。项目团队编制16人，薪酬福利高于同类周边项目，一线人员全部直招不外包。针对老旧项目提出四步举措：洗理静音（进场第一个月调动湖南战队资源全面清扫环境绿化）、疏金活选（调动集团设备公司工程师全面排查诊断设备设施）、疑难杂症（涉及重大改造通过业委会授权或业主大会招投标）、有效提升（导入公司管理标准和特色系统）。资平物业还将导入顾客管理系统，集中处理业主投诉咨询报事，形成大数据指导后续工作，并针对老龄化开展社区文化活动，每两个月开展一次。
+## 00:19:52-00:34:44 资平物业答疑
+业主代表向资平物业提出五个问题。关于改造计划，资平物业表示经查勘发现小区主要存在安全管控、设备设施维护、环境和社区氛围四方面问题，进场第一个月集中整改环境绿化，半年内处理设备设施，八个月内完成主要改造，一年内达到有序状态。关于包干制经验，资平物业介绍其在湖南有11个项目，其中10个为包干制、1个为酬金制，强调包干制下同样保证财务透明和业主知情权，团队30%来自现有优秀员工，60%左右来自现有物业优秀员工或新招聘；公益服务方面提供居家上门服务（员工免费，材料费业主自付或代购）、家政及24小时业主护送服务。关于承接查验，资平物业强调前期准备充足，与社区街道派出所沟通、与原物业和业委会明确设备设施及债务债权，按专业线分组验收并委派集团工程师协助，增派150%人员参与承接查验。关于安防停车，资平物业提出关键岗位（门岗、门勤岗、车务）用老员工，收集业主车辆信息制定停车管理方案，升级道闸系统识别外来人员，通过技术手段加强监控。关于楼层顶层杂物和乱晾晒，资平物业提出宣传法律知识、联合社区应急管理部门、上门沟通并限期处理、设置临时堆放区（限期解决）、设置集中晾晒区，强调“疏”而非“强制”，避免激发矛盾。
 ## 00:35:00-00:35:28 评标结果公布
-业主代表宣布所有答辩结束，评标委员会进行打分，打分环节全程保密，暂停会场网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。随后公布各公司得分：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源新东源物业管理有限公司54.48分，中标候选人为深圳市资平物业发展有限公司，招标活动圆满结束。
+评标委员会完成打分，主持人宣布打分环节全程保密、暂停网络直播、录像材料不予公开，评标打分去掉一个最高分和最低分。最终公布结果：第一名（中标候选人）为深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源新东源物业管理有限公司54.48分。主持人宣布深圳市资平物业发展有限公司中标，招标活动圆满结束。
 # 要点梳理
-## 富家物业答疑
-- **改造计划**：富家物业预计改造时间在一年内完成，具体12大改造点已在标书第117页详细说明。
-- **停车乱象应对**：先分析乱停原因（场地不足、距离远或不自觉），若车位不足则增加停车位，若业主不自觉则派保安、客服现场说服、劝阻、纠正。
-- **承接查验安排**：提前两周项目负责人入场摸底小区现场情况；提前一周服务人员到位并培训公司制度与操作流程。
-- **交接不畅应对**：先与现物业私下沟通了解诉求，公司间能解决则解决；无法解决则请业委会或街道社区组织现场协调会；仍无法解决时，在业委会、业主大会及街道社区许可下采取强制措施。
-- **安防改善措施**：大门口增设人行门禁系统（支持手机微信、卡、密码进出）；升级大堂报到系统，录入业主车辆信息统一管理，临时车辆由安保登记后放行；地面增设隔离墩禁止公共场所停车，保障消防通道与人行通道畅通；建设外围停车场并安装停车管理系统；小区内增设电动车停车场。
-- **业主问题处理原则**：采用「用心倾听、如实记录、马上处理、及时反馈」四句话，处理完成后及时向业主反馈完成时间。
-## 知名管理答疑
-- **公司背景**：知名管理成立于2004年，总部在深圳，为全市场化物业公司，无开发背景；全国367个项目，其中127个为业委会项目；公司创始人陈志平为万科物业创始人，曾协同建立中国第一个业委会；公司为中国物业管理协会副会长单位、全国百强企业。
-- **团队配置**：景城苑项目团队编制16人，薪酬福利保证高于周边同类项目；所有一线人员直招不外包。
-- **进场改造计划**：四步举措——第一步「洗理静音」，进场第一个月调动湖南战队其他项目人员资源，对小区环境、绿化、清洁、杂物进行全面清扫；第二步「疏金活选」，调动集团设备公司水电、给排水、电梯、消防工程师对设备设施全面排查诊断，在投资范围内集中改造；第三步「疑难杂症」，涉及消防、渗水等重大事项检查后提供意见，经业委会授权或业主大会招投标；第四步「有效提升」，将总部管理标准与经验延续至本项目，八个月内保证项目有效运作。
-- **包干制经验**：长沙11个项目中10个为包干制、1个为酬金制；包干制下保证财务透明，每季度公示物业管理费、停车费；管理透明，业委会授权事项推进业主代表参与公共事务管理；团队30%管理干部从现有人员选拔，60%左右为现有物业优秀员工或重新招聘。
-- **公益与增值服务**：长沙项目居家上门服务员工免费，材料费由业主自买或物业代购；开展家政、24小时业主护送服务等有偿与无偿业务。
-- **承接查验安排**：前期与社区、街道、派出所沟通；与现物业、业委会明确设备设施、债务债权；按专业线分专业组验收，委派集团工程师协助查出问题；在现有16人团队基础上增派150%人员参与承接查验。
-- **安防与停车管理**：门岗、门勤岗、车务等关键岗位用老员工，对来访人员与车辆进行管控、登记、核实后放行；收集小区业主车辆信息，制定整体停车管理方案（含禁区停放、动线规划）；升级门禁系统识别外来人员与业主亲戚来访；通过设备公司技术手段对关键岗位与关键部位监控进行梳理把控。
-- **楼层杂物处理**：通过上门宣传、海报、法律知识宣传引起业主重视；与社区、应急管理部门联合行动；逐户沟通说明危害，给予业主处理杂物的时间段；可提供闲置区域供业主临时堆放并限期解决；强调「疏导而非强制」，避免激发矛盾。
-- **晾晒问题处理**：计划在小区寻找位置设置集中晾晒区；可提供免费增值服务，太阳大时物业工作人员上门取送晾晒物品（早上拉出、晚上拉回）。
+## 富佳物业应答
+- **改造计划**：富佳物业预计改造时间在一年内完成，具体12大改造点在标书117页有详细说明。
+- **车辆乱停应对**：先分析乱停原因（停车位不够、停车位置太远、业主不自觉），再针对性制定措施——停车位不够则增加停车位，业主不自觉则派保安、客服人员现场说服、劝阻、纠正。
+- **承接查验安排**：提前两周项目负责人入场摸底小区现场情况；提前一周服务人员安排到位并培训公司制度与操作流程。
+- **交接不畅应对**：先与原物业私下沟通了解诉求，公司间能解决则自行解决；不能解决则请业委会或街道社区领导组织现场协调会；仍不能解决时，在获得业委会、业主大会及街道社区许可下采取强制措施。
+- **安防与停车整改**：大门口增设人行门禁系统（支持手机微信、卡、密码进出）；升级大堂报到系统，录入业主车辆信息统一管理，临时车辆由安保人员登记后放行；地面增设隔离墩，禁止公共场所停车，保障消防通道与人行通道畅通；建设外围停车场并安装停车管理系统；小区内增设电动车停车场（考察发现电动车乱停与停车位不足有严重关系）。
+- **业主满意度与收费率**：采取四句话方法——用心倾听、如实记录、马上处理和及时反馈，处理完成后及时向业主反馈完成时间，业主可联系确认。
+## 资平物业应答
+- **公司概况**：资平物业（知名管理）成立于2004年，总部在深圳，全市场化物业公司、无开发背景；全国367个项目，其中127个业委会项目；公司陈志平先生原为万科物业创始人，曾协同建立中国第一个业委会；公司为中国物业管理协会副会长、全国百强企业。
+- **管理原则**：所有业委会项目财务透明，包干制下每季度对全体业主公示物业管理费、停车费等财务；管理透明，推进业主代表参与小区公共事务管理。
+- **团队配置**：景城苑项目人员配置16人；薪酬福利保证高于同类及周边项目；所有一线人员直招不外包（长沙经验教训显示外包对现场服务品质影响大）。
+- **老旧项目四步举措**：①洗理静音——进场第一个月调动湖南战队其他项目人员资源，对环境绿化、杂物进行全面清扫，保证感官上干净整洁有序；②疏金活选——调动集团设备公司水电、给排水、电梯、消防工程师，对小区设备设施全面排查诊断，在投资范围内集中改造；③疑难杂症——涉及消防、渗水等重大问题，检查后提供意见，经业委会授权或召开业主大会进行招投标；④有效提升——将总部管理标准与经验延续到项目，保证八个月以内项目有效运作。
+- **管理系统导入**：全面导入顾客管理系统，业主投诉、咨询、报事集中到系统，设专线电话，保证有人跟进、有人回访；根据每月业主投诉报事数据形成大数据库，指导下月工作方向（如10月业主对门岗管控有意见，11月重点改善）。
+- **社区文化活动**：根据小区老龄化导入巡产活动，教老年人使用抖音；根据小区不同团体（跳舞、打篮球等）做小区社团；公司硬性标准为每两个月开展一次社区文化活动。
+- **改造时间计划**：进场第一个月集中整治环境绿化（补种绿化、清理楼道杂物、牛皮癣等）；半年内处理设备设施；八个月内完成主要改造；一年内保证小区达到有序状态。
+- **包干制经验**：资平物业在湖南有11个项目（长沙11个），其中10个包干制、1个酬金制；包干制下保证业主知情权、阳光透明实施，增加与业委会、业主互动，让业主参与物业管理。
+- **团队构成**：管理干部30%来自集团现有优秀员工，60%左右来自现有物业优秀员工或重新招聘。
+- **公益服务**：长沙所有项目居家上门服务员工免费，材料费业主自买或物业代购；开展家政、24小时业主护送服务等有偿和无偿业务。
+- **承接查验安排**：前期与社区、街道、派出所沟通；与现有物业、业委会坐下来明确设备设施、债务债权等事项；按专业线分专业组验收（消防、漏电、监控门禁等），调动集团工程师协助查出问题；在现有16人团队基础上增派150%人员协助承接查验与数字化工作。
+- **安防与停车整改**：关键岗位（门岗、门勤岗、车务）用老员工，保证责任心与担当意识，对外来人员车辆进行管控、登记、核实后放行；收集小区业主车辆信息，制定整体停车管理方案（含禁区停放），升级道闸系统识别外来人员与业主亲戚来访；通过设备公司从技术层面解决关键岗位、关键部位监控问题。
+- **楼层顶层杂物处理**：宣传引导——上门宣传、小区海报、法律知识宣传，让业主明白堆放杂物有风险且需承担法律责任；联合社区、应急管理部门采取行动；上门沟通告知危害，给业主时间段处理杂物；物业可提供闲置小区域供业主临时堆放（贴纸条注明临时堆放、限期解决）；强调“疏”而非“强制”，避免激发矛盾。
+- **晾晒问题处理**：在小区寻找位置建集中晾晒区供业主晒被子；可提供增值服务——太阳大时物业工作人员免费上门取送晾晒物品（早上拉出、晚上拉回）。
 ## 结论与决定
-- **评标结果**：评标委员会打分后确定中标候选人为深圳市资平物业发展有限公司。
-- **各公司得分**：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源新东源物业管理有限公司54.48分。
-- **打分规则**：总评委打分去掉一个最高分和一个最低分；打分环节全程保密，暂停会场网络直播，录像材料不予公开。
+- **中标结果**：深圳市资平物业发展有限公司为中标候选人（第一名）。
+- **评分结果**：第二名长沙富佳物业管理有限公司72.91分；第三名湖南恒居恒基居业物业管理有限公司60.73分；第四名重庆新东源新东源物业管理有限公司54.48分。
+- **评标规则**：打分去掉一个最高分和最低分；打分环节全程保密，暂停会场网络直播，录像材料不予公开；评委、监督员及必要会务人员以外人员退场。
 ## 待确认与风险
-- **停车管理**：小区存在车辆停放不规范、电动车乱停现象，卫生室区域同样存在此类问题。
-- **安防隐患**：监控门禁失效导致人员车辆随意进出，小区停车管理混乱。
-- **消防通道占用**：消防通道停放车辆较多，含业主车辆及外来车辆。
-- **楼层杂物**：楼层顶层存在堆放杂物或乱搭乱晒问题，涉及业主生活与安全影响。</t>
+- **车辆停放**：小区存在车辆停放不规范、电动车乱停现象，卫生室区域同样存在此类问题。
+- **安防隐患**：监控门禁失效，导致人员车辆随意进出。
+- **停车管理**：小区停车管理混乱，消防通道停放车辆（含业主车辆及外来车辆）。
+- **楼层隐患**：楼层顶层存在堆放杂物、乱搭乱晒问题，涉及业主生活与安全影响。</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>48</v>
+        <v>58.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11743/4252</t>
+          <t>11743/4382</t>
         </is>
       </c>
     </row>
@@ -12626,58 +12657,63 @@
       <c r="C35" t="inlineStr">
         <is>
           <t># 讲座概况
-本期视频由主讲人李正（B站「正直讲史」）讲述康熙朝文渊阁大学士陈廷敬的一生，形式为历史人物专题讲解。视频旨在澄清影视剧与史实的差异——剧中陈廷敬支持撤藩、招抚台湾、征剿噶尔丹等功绩均非史实，但康熙临终前仍询问大臣中学问人品如陈廷敬者可代理内廷事务者为谁，由此引出其生平。内容按三个阶段展开：妈妈张氏的开蒙、圣祖康熙的讲师、至公无私的落幕。核心主张有三：其一，陈廷敬虽无影视剧中的显赫功绩，却凭清廉正直与恪守初心赢得康熙终身信任；其二，其童年由母亲张氏开蒙，6岁前已背诵《论语》《孟子》《大学》《中庸》《诗经》，天赋与家教奠定一生根基；其三，宦海浮沉50年声名清白，历经张谦案诬陷仍获康熙力挺复出，印证「清者自清」。关键锚点包括：陈廷敬1638年生于山西泽州府阳城县，21岁中进士入翰林，75岁病逝谥号文贞。对听众而言，本讲以具体人物案例展现清代官场生态与个人操守的张力，适合对清史、古代政治人物及廉政主题感兴趣的观众。
+本期视频由主讲人李正讲述康熙朝文渊阁大学士陈廷敬的一生，以「妈妈张氏的开蒙」「圣祖康熙的讲师」「至公无私的落幕」三个阶段为骨架，旨在澄清影视剧虚构功绩（支持撤藩、招抚台湾、征剿噶尔丹均非史实）的同时，还原陈廷敬凭何让康熙临终仍念念不忘。核心主张有三：其一，陈廷敬由母亲张氏开蒙，6岁前已背诵《论语》《孟子》《大学》《中庸》《诗经》，14岁以童子第一入州学，21岁中进士入翰林；其二，他任经筵讲师期间教学风格外放、讲评狠辣，并因整顿国子监、左都御史任上严查捐纳与赈灾而屡获康熙支持；其三，历经亲家张谦贪污攀咬案后辞官复出，康熙再任其为左都御史，以行动宣告其清白，晚年四次请退方获准，谥号文贞。讲座面向历史爱好者与关注清代官场文化的观众，以陈廷敬「知世故而不世故」的一生，说明品行端正对从政的根本意义。
 # 核心观点与论证
 ## 母亲张氏开蒙奠定根基
-- **开蒙方式**：陈廷敬6岁外出上学前，由母亲张氏口授背诵《论语》《孟子》《大学》《中庸》《诗经》，史载“凡四子书毛诗皆太夫人口授以诵”。
-- **母亲背景**：张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，史载“太夫人少儿颖慧特异……无不背诵通晓大义”；嫁后“于家政稍暇即出书籍……非秉夜不归寝”。
-- **鼓励教育**：陈廷敬9岁作《咏牡丹》，其中“要使误接春”一句被母亲赞为“天才”，童年学习大半在母亲关照下展开。
-- **科举成绩**：顺治八年（1651年）14岁以全省第一考中秀才；20岁中举人，21岁中进士并入翰林院任庶吉士，同年入选翰林院。
-## 御赐改名化解重名风波
-- **重名事件**：顺治15年（1658年）四月，山西泽州陈敬与直隶通州陈敬同届中进士入翰林院为庶吉士，因满汉双语文件与考试造成混淆。
-- **他人连累**：直隶陈敬因满文考试不及格被顺治点名批评并罚俸一年，原话“陈敬……清书俱未习熟……着各罚俸一年”，因未带籍贯导致风言风语波及陈廷敬。
-- **主动改名**：陈廷敬22岁主动上书请更名，史载“庶吉士陈敬奏请更名廷敬，以与直隶庶吉士陈敬同名故也”。
-- **御赐之名**：据李光地说，“廷”字为顺治所赐，原话“陈文贞公初名敬，其家廷字文选日张皇帝所赐也”，改名后与顺治拉近关系。
-## 康熙讲师与教学风格
-- **仕途晋升**：康熙六年（1667年）考察一等称职；两年后32岁升任正六品国子监司业；34岁升从四品翰林院侍讲学士；35岁充日讲起居注官；39岁充经筵讲官。
-- **整顿国子监**：陈廷敬任国子监司业时废除学生拜见须带见面礼的不成文规定，史载“凡诸生以至献者悉秉去之”，学生不送礼才愿意见。
-- **教学风格**：讲评经史“特别狠辣，对就骂错就骂”，曾指史书痛骂孙权背刺关羽，原话“全其屯权也哉”，康熙欣赏其坚定三观与外放风格。
-- **执掌翰林院**：康熙16年（1677年）正月任翰林院掌院学士，教习当届庶吉士。
-## 至公无私整顿吏治
-- **捐纳考试**：康熙23年（1684年）47岁任左都御史，上奏捐纳买官者正式上岗须追加考试，“文艺略小者给予录用，否则且令异业听其再试”；吏部反对称“以前补用人员从未考试，应不准行”，康熙支持并令各地督抚详查已任命官员，“凡临民之官内有不识字义者，着该督府不时实行查参修治”。
-- **全面弹劾**：针对各省督府作风问题、地方政府赈灾懒政问题严查弹劾，并亲自拟定新的赈灾报批流程；两年内连续出任工部、户部、吏部三部尚书，所到之处整顿得罪人。
-- **个人立场**：面对“官场里不和光同尘会落满怨”的劝告，陈廷敬表示“我贤与虽折且怨，庸和尚说”，只要人是对的、事是好的，遭受挫折埋怨也无所谓。
-## 张谦案与清白复出
-- **被诬受贿**：康熙26年（1687年），湖广巡抚张谦（陈廷敬老乡兼亲家）贪污被抓，供称曾贿赂徐乾学、高士奇及陈廷敬，证据是三人曾写信劝其好好当官，被张谦解读为索贿暗示。
-- **自辩与辞官**：陈廷敬称“前楚府一案者……积疑成恨，羽射连染”，因对张谦疏远反遭怨恨攀咬；51岁主动上书辞官，康熙准许但留京修书。
-- **康熙定调**：康熙传旨主审官马齐“此时需旧款需问，不可蔓延，若蔓延则千累者重”，只处理张谦一人，其余事后密查。
-- **清白佐证**：主讲人给出三点理由——据李光地说张谦案从索贿到举报皆徐乾学一手策划；徐乾学贪污事迹多且热衷结党；徐乾学、高士奇后来均因贪污被罢官，唯独陈廷敬康熙29年（1690年）53岁复出再任左都御史，康熙以任命全国最高监察长官宣告其清白。
-## 晚年请退与身后哀荣
-- **官至大学士**：康熙42年（1703年）66岁升任文渊阁大学士，同时总理南书房事务，是内阁中唯一既管南书房又任经筵讲师的大学士。
-- **四次请退**：70岁起连续三年三次申请退休均被康熙拒绝，康熙称“机务重地，良难其人，不必求去”；73岁第四次申请获准。
-- **御赐匾联**：康熙赐匾额“午亭山村”和楹联“春归乔木浓阴茂，秋到黄花晚”，并称“自此不与人写字矣”。
-- **病逝与厚葬**：康熙49年（1710年）后两年，陈廷敬75岁病逝，谥号文贞；康熙包办治丧费用，从大内取紫砂碗做棺材，命皇三子允祉及大臣侍卫往吊，令各部院满汉大臣往吊。
+- **家世背景**：陈廷敬本名陈敬，字子端，号午亭，1638年（崇祯十一年）出生于山西泽州府阳城县，家中书香门第，往上数六代都是读书人且多在朝廷为官；父亲陈长七虽为管理家业未走仕途，但入选过顺治朝国子监。
+- **母亲张氏的教育**：张氏自幼随父亲张弘毅读书，通晓儒家经典与《资治通鉴》，嫁给陈廷敬父亲后仍每日读书背诵至半夜；陈廷敬6岁外出上学前，已由母亲口授背完《论语》《孟子》《大学》《中庸》《诗经》。
+- **天赋与鼓励**：陈廷敬9岁作《咏牡丹》，母亲张氏夸其“天才”；主讲人指出陈廷敬学习天赋大概率遗传自母亲，因其父陈长七在儿子17岁那年才考上贡生。
+- **科举成绩**：顺治八年（1651年）陈廷敬14岁以童子第一入州学，20岁中举人，21岁中进士并入翰林院任庶吉士；主讲人对比称“天才如李光地，21岁时连秀才还没考上”。
+## 入翰林与改名风波
+- **重名事件**：顺治十五年四月，陈廷敬与直隶通州陈敬同榜中进士并选为庶吉士；直隶陈敬因满文考试不及格被顺治点名批评并罚俸一年，但顺治未带籍贯，导致陈廷敬受流言牵连。
+- **主动改名**：陈廷敬22岁时主动上书顺治请求改名“廷敬”，以与直隶庶吉士陈敬区分；据李光地记载，“廷”字为顺治所赐。
+- **仕途顺遂**：顺治十八年，陈廷敬24岁在庶吉士毕业考试中获同届第一，授秘书院检讨；顺治与陈廷敬同为崇祯十一年出生，顺治欣赏陈廷敬，其在翰林院“如鱼得水”。
+## 为母守孝与康熙讲师
+- **请假归乡**：康熙元年，陈廷敬收到母亲张氏病重消息，在仕途起步关键时刻请假归乡三年；母亲病愈后，陈廷敬康熙六年获考察一等称职，康熙八年32岁升任国子监司业。
+- **整顿国子监**：陈廷敬任国子监司业时废除学生拜见须带见面礼的不成文规定，学生越送礼越不见，不送礼才愿见；两年内连升三级，34岁任翰林院侍讲学士。
+- **担任讲师**：康熙十一年十月，陈廷敬35岁充日讲起居注官；康熙十五年九月，39岁以内阁学士兼礼部侍郎充经筵讲官；康熙十六年出任翰林院掌院学士，给当届庶吉士上课。
+- **教学风格**：陈廷敬讲评经史“特别狠辣，对就骂错就骂”，曾指史书骂孙权“全其屯权也哉”，认为吴蜀唇齿相依，孙权背刺关羽“简直就是猪是狗”。
+## 母亲去世获康熙特旨祭奠
+- **母亲病逝**：康熙十六年，陈廷敬母亲张氏因病去世，终年59岁；陈廷敬立刻请假回乡奔丧。
+- **打破满汉界限**：康熙召集大臣表态，称“满汉大臣俱系一体”，汉大臣有丧亦应遣大臣往祭，命大学士明珠、翰林院掌院学士喇沙里携茶酒往祭。
+- **礼部反对与康熙坚持**：礼部以陈廷敬母亲封号系詹事府詹事时授予、按例不得祭奠为由反对；康熙回应“以平靖侍从勤劳而恩弗待，吾何以劝劳臣乎”，下令追封陈廷敬母亲按学士品级由官方祭奠。
+## 左都御史整顿吏治
+- **捐纳考试**：康熙二十三年，陈廷敬47岁升任左都御史，上奏捐纳买官者上岗前须追加考试，“文艺略小者给予录用，否则且令异业听其再试”；吏部反对称“以前补用人员从未考试”，康熙支持陈廷敬并令各地督抚详查已任命官员，凡不识字义者“不时实行查参修治”。
+- **全面弹劾**：陈廷敬针对各省督府作风问题、地方政府赈灾懒政问题严查弹劾，一边指出问题一边给出解决方案，亲自拟定新的赈灾报批流程。
+- **三部尚书**：随后两年陈廷敬连续出任工部、户部、吏部三部尚书，“他人到哪里就整顿到哪里”；面对劝其“和光同尘”的建言，陈廷敬表示“我贤与虽折且怨，庸何伤”，只要人是对的、事是好的，遭受挫折和埋怨也无所谓。
+## 张谦案牵连与清白复出
+- **案件经过**：康熙二十六年，湖广巡抚张谦因贪污被抓，张谦系陈廷敬老乡兼亲家（其子是陈廷敬二女婿）；张谦供称曾贿赂陈廷敬、徐乾学、高士奇，并拿出三人劝其好好当官的信件作为“索贿暗示”证据。
+- **陈廷敬自辩**：陈廷敬否认受贿，称因张谦是亲戚自己尤其注意、从未特殊往来，张谦是因自己过于疏远而产生怨恨、恶意攀咬；康熙传旨主审官马齐“只处理张谦一个人，不得扩大株连”，其他人等事后密查。
+- **辞官与复出**：康熙二十七年，陈廷敬51岁主动上书辞官，康熙准许但留京修书；康熙二十九年，陈廷敬53岁复出再任左都御史。
+- **清白依据**：主讲人个人倾向陈廷敬无辜，理由三点：①据李光地记载，张谦案从索贿到举报皆由徐乾学一手策划；②徐乾学贪污事迹多且热衷结党；③徐乾学、高士奇后来均因贪污被罢官，唯独陈廷敬仅辞官一年即被康熙重新启用任全国最高监察长官。
+## 晚年高位与四次请退
+- **位极人臣**：康熙四十二年，陈廷敬66岁升任文渊阁大学士，总理南书房事务；任大学士期间是内阁中唯一既管南书房又当经筵讲师定期给康熙上课的人。
+- **四次请退**：康熙四十六年起，陈廷敬70岁开始申请退休，连续三年被拒，康熙称“机务重地，良难其人，不必求去”；康熙四十九年，73岁第四次申请退休获准。
+- **御赐匾联**：康熙亲写匾额“午亭山村”和楹联“春归乔木浓阴茂，秋到黄花晚节香”，并称“朕特殊匾联赐卿，自此不与人写字矣”。
+- **病逝与哀荣**：两年后陈廷敬病逝，终年75岁，谥号文贞；康熙包办治丧费用，从大内找紫砂碗做棺材，命皇三子允祉及大臣侍卫往吊，各部院满汉大臣往吊。
 # 金句总结
-&gt; 朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？
-- 康熙在陈廷敬临终前询问，还有谁可代理内廷事务，足见对其倚重之深。
-&gt; 自古未有不晓文艺之人可以为民父母者也，有未经考职遂行捐纳者，于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试。
-- 陈廷敬任左都御史时上奏，主张捐纳买官者正式上岗前必须追加考试，获康熙支持。
-&gt; 臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节。
-- 张谦案中被攀咬后，陈廷敬主动上书辞官以证清白。
-&gt; 苟正其身矣，于从政乎何有？
-- 主讲人引《论语》总结陈廷敬一生：自身品行端正，治理政事便无困难。
-&gt; 我贤与虽折且怨，庸和尚说只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，你也是无所谓的。
-- 有人劝陈廷敬官场应和光同尘时，他回应只要行得端做得正，不怕挫折与埋怨。
+&gt; “朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？”
+- 背景：康熙在陈廷敬临终前询问，朝中是否还有像他一样可代理内廷事务的大臣，足见对其倚重之深。
+&gt; “要使误接春，定须春恨事。”
+- 背景：陈廷敬9岁作《咏牡丹》，母亲张氏读后夸其为“天才”，此为其童年受母亲开蒙鼓励的例证。
+&gt; “自古未有不晓文艺之人可以为民父母者也。”
+- 背景：陈廷敬任左都御史时上奏，主张捐纳买官者正式上岗前必须追加考试，考不上不得任职。
+&gt; “我贤与虽折且怨，庸和尚说只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，你也是无所谓的。”
+- 背景：陈廷敬连任三部尚书、到处整顿得罪人后，有人劝其和光同尘，他以此回应，表明知世故而不世故的立场。
+&gt; “臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节。”
+- 背景：张谦案中陈廷敬被攀咬受贿，为证清白，51岁时主动上书辞官。
+&gt; “苟正其身矣，于从政乎何有？”
+- 背景：主讲人引用《论语》总结陈廷敬一生——自身品行端正，治理政事便无困难，其儿时所学道理至死未违。
 # Q&amp;A 环节
 未提及</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>60.9</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9132/2677</t>
+          <t>9132/3109</t>
         </is>
       </c>
     </row>
@@ -13298,63 +13334,62 @@
       <c r="C36" t="inlineStr">
         <is>
           <t># 访谈概述
-本期《锵锵三人行》围绕刚播完的日剧《大奥》与明朝历史展开，受访者为《明朝那些事》作者当年明月（笔名），与主持人及另一位嘉宾共同探讨中日文化差异与历史认知。访谈主线分两大板块：一是由《大奥》切入日本文化，覆盖该剧反映的日本历史阶段、大奥制度、日本民族精神中的极端精神与忠诚文化、战后经济崛起及中日文化差异；二是转向明史，讨论明史为何吸引人、朱元璋的历史地位、明朝兴亡经验、晚明市民生活及明式家具等话题。受访者核心观点包括：日本文化强调极端精神，做事做到尽头，战后仅用30年成为世界第二经济强国（绝对量而非人均量），是强国中唯一没有资源的国家；中国文化的核心精神是中庸，日本则坚持做到极致，二者差异巨大；历史事件发生时有背景，后人并不比前人聪明，「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」。访谈看点在于当年明月以《大奥》为引，结合其亲历的日本豆腐厂参观（夜里12点整准时开工）等细节，指出日本人的严谨与忠诚文化，并直言正德皇帝「绝不是史料上所写的那么蠢」，认为其被嘉靖朝修史者写坏。
+本期《锵锵三人行》由主持人窦文涛与《明朝那些事儿》作者当年明月、嘉宾马未都围绕日剧《大奥》展开对谈，听众参与讨论。话题从《大奥》三部曲切入，前两部对应中国晚清到清初，第三部在明治维新之前；大奥即后宫，日语“奥”指屋子最深处。嘉宾认为该剧体现日本文化的严谨与极端精神，并延伸至日本战后30年以绝对量成为世界第二经济强国、唯一没有资源的强国，以及终身雇佣制下仍保持高效率等话题。对谈随后转入明朝历史与《明朝那些事儿》：当年明月表示明史资料最多但一个事件可能有七个不同说法，研究难点在于史料庞杂且相互矛盾；他推崇朱元璋，认为其是历史上唯一由最底层乞丐当上皇帝的人，明朝规章制度基本由其定下且无大改动。嘉宾讨论明末江南市民生活富裕、工商业兴起、出现三言二拍等市民小说，以及明末陕西灾荒引发李自成起义、吴三桂以替崇祯复仇为名入关、1644年北京爆发疙瘩瘟（可能为天花）等史实。关于明朝皇帝评价，嘉宾认为正德皇帝被嘉靖指派杨廷和等人编纂的《明武宗实录》写坏，其从江南回京在通州停半年先打探京城情况，显示有城府；天启皇帝爱当木匠，干完活拆大盆去卖，反映当时社会时尚，明式家具在国际上地位高并非偶然。马未都还对比宋明汉人文人政权与满族异族政权的审美差异，认为前者审美素雅、后者偏重表象。
 # 访谈详细记录
 ## 日剧《大奥》与日本文化
-- **《大奥》历史阶段**：受访者认为该剧三部曲中，前两部大致对应中国晚清到清初时段，第三部在明治维新之前，是一部有跨越性的历史剧。
-- **大奥释义**：受访者指出大奥即普通话所说的后宫，日语中"奥"指很深的地方，即屋子最里处，如"深奥"一词仍保留此痕迹。
-- **日本极端精神**：受访者认为从《大奥》可看出日本文化从头到尾未变，其特点是"极端精神"——所有事情要做到尽头，如剧中所有演员达成一致、人人认真，具有专业精神。
-- **战后经济奇迹**：受访者认为日本战后用30年成为世界第二经济强国（绝对量而非人均量），不是偶然而是必然，源于全民族极端精神；日本是世界上强国里唯一没有资源的国家。
-- **忠诚文化体现**：受访者以剧中阿福为例——25岁进大奥当奶妈，65岁去世，40年无论做什么事不处私心、完全是公心，被伤害的对方都认为他出于公心，这是日本忠诚文化的具体体现。
-- **豆腐厂细节**：受访者讲述参观日本最底层豆腐厂的经历——规定当天做当天卖，夜里11:45所有人坐等看表，12点整准时开工，4点多干完上市，无人闲聊胡侃。
-- **做绳子的商人**：受访者举例日本做绳子做到全日本第一的人，几年内不赚钱，从批发到送货1分钱不赚，等铺平市场后拿单据要求加2%，全国加起来4%即挣大钱。
-- **中日文化差异**：受访者认为中国文化精神是中庸，讲究融合、走最适合的路；日本精神恰恰相反，坚持一个原则做到极致，如炮手忘记一切只记得把炮开出去即达最高境界。
-- **终身雇佣制**：受访者指出日本实行终身雇佣制，按经济学原理缺乏竞争应导致低效，但日本终身雇用下效率依然特别高，是经济学上的奇迹。
-- **日本生存环境**：受访者认为日本没有资源、常火山地震，人对世界有极强求生欲望或悲观感，必须融入团体按固定规则做事才能生存；受访者认为日本"聪明人"没有生存环境，社会文化抵制非常难过。
-- **对死亡的看法**：受访者认为日本人看樱花只看落的那天，因岛国生态环境恶劣，对死亡不是藐视而是有点向往或不惧怕，二战日军在华暴行源于藐视生命；另一受访者不同意，认为日本民族不是藐视生命而是重视，经济危机时很多身家万贯者选择自杀。
-- **是否愿做日本人**：受访者表示不愿做日本人，因其很多时候像盲从，且有寻死的潜在欲望；另一受访者认为每个人在自己文化环境里愿意做，但做不成，因为自己的文化不允许这种现象生存。
+- **《大奥》剧情阶段**：该剧共三部，前两部对应中国晚清到清初时段，第三部在明治维新之前，是一部有跨越性的历史剧。
+- **大奥释义**：大奥即普通话所说的后宫，日语中“奥”指很深的地方、屋子最里处，如“深奥”一词即保留此痕迹。
+- **受访者认为《大奥》体现日本人的严谨精神**：剧中每个群众演员都非常认真、有专业精神，看不到笑场；第一集片头将军出场时所有人呈45度鞠躬，场面华丽、色彩讲究，一看就不一样。
+- **受访者认为日本文化核心是极端精神**：所有事情要做到尽头，发自内心地一致；战后1945年日本用30年以绝对量（非人均量）成为世界第二经济强国，且是世界上强国里唯一没有资源的国家，这不是偶然而是必然。
+- **受访者对比中日文化精神**：中国文化精神是中庸，讲究世界上有一种道，不是对也不是错、不是黑也不是白，是一条最适合的路；日本精神恰恰相反，坚持一个原则，如炮手忘记所有事情只记得把这一炮开出去，就达到最高境界。
+- **受访者谈日本忠诚文化**：日本是忠诚文化的典型国家，强调忠诚、守本分；《大奥》中阿福25岁进大奥当奶妈，65岁去世，40年无论做什么事不处于私心、完全是公心，被伤害的对方都认为他是出于公心。
+- **受访者谈终身雇佣制**：日本实行终身雇佣制，按经济学原理缺乏竞争必然导致低效，但日本终身雇佣下效率仍然特别高，是经济学上的奇迹。
+- **受访者举例日本豆腐厂**：日本豆腐规定当天做当天卖，夜里11:45所有人做好不动手坐着看表，12点整一到赶紧开车干活，4点多干完上市，没人闲聊胡侃。
+- **受访者举例日本做绳商人**：有人做绳子做到全日本第一，几年内不赚钱，从批发到送货1分钱不赚，等市场铺平后拿两张单子各加2%，全国的东西4%就是不得了的利润。
+- **受访者认为日本民族不藐视生命而是重视**：日本人在经济危机时很多身家万贯者选择自杀，不是藐视生命，而是重视生命这个资本。
 ## 明朝历史与《明朝那些事》
-- **写明史的原因**：受访者（当年明月）表示写明朝是因为明史资料最多；历史研究有两个难点，一是先秦（如孙武事迹在史记仅一两篇，多为编撰），二是明清——明史录几千万字、明通鉴、明史记事本末、明会典等堆得比山还高，但一个事件可能有七个不同说法，如同罗生门。
-- **明朝的跌宕起伏**：受访者认为明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变（皇上被瓦剌军抓走）、夺门之变等，各种"之变"特别多，构成现代版电视剧般离奇情节。
-- **推崇朱元璋**：受访者认为朱元璋是历史上唯一由最底层（乞丐）当上皇帝的人，刘邦好歹算村长或乡长；要过饭的人当上皇帝，每一层的猫腻全知道，因此疑心重；明朝规章制度由朱元璋定下，基本无大改动。
-- **英雄史观**：受访者认为人的因素最大，改变时势一定出现一个人；朱元璋天分相当高，如同《亮剑》中李云龙没上过军事院校却能打仗，是战场上死死生生积累的经验。
-- **朱元璋起义的逼上梁山**：受访者讲述朱元璋原在庙里犹豫是否参加起义军，因信差送信被人听到告发，没办法只能去起义；受访者强调历史最重要的是明白它是发生过的，旁观者觉得好玩，但当事人是掉脑袋的风险。
-- **历史经验教训**：受访者认为"我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训"，因为历史事件发生时有背景，你不比前人聪明，甚至可能比前人笨，那种情况出现时你也得这么办。
-- **史书如照片**：受访者比喻史书记载下来的是照片，而古人的生活是录像，你不知道那一幕之前和之后是什么，所以不能套用历史经验教训。
-- **晚明市民生活**：受访者认为明末很多真相被掩盖，江南一带市民生活特别轻松，想去哪去哪，皇册都不用，给人当雇工，工商业兴起，三言二拍这类市民小说出现说明有养活自己的资本；李自成起义时陕西一带发生大规模灾荒。
-- **明末工艺与艺术**：受访者指出明末工艺品变得非常精细，日本派大量工匠来交流学习；吴门画派文徵明、唐寅等画小桥流水、风雨归舟图，充满欣赏感觉，说明生活好；到八大山人朱耷时画翻白眼，因对社会愤愤不平。
-- **明朝灭亡的蹊跷**：受访者提到1644年明朝灭亡那年北京闹瘟疫（疙瘩瘟，可能是天花），李自成打到京城无人抵抗；受访者与老师交流认为明朝亡得真蹊跷，什么坏事都赶上了。
-- **王朝300年大限**：受访者认为中国历史王朝300年是大限，逼近300年自己就没了，和人到八九十岁大限快到一样；严格讲超过300年的只有宋朝（南北宋接上，退让大半个国土），汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
-- **明朝的趣味**：受访者认为明朝什么都有——宦官专政（魏忠贤）、文官专政（张居正）、皇帝专政（朱元璋），皇帝出去了还能回来、回来了还能做皇帝；吴三桂与满清合作入关，除陈圆圆外还因崇祯死了，当时说法是"入关为崇祯皇帝复仇"。
-- **正德皇帝被写坏**：受访者认为正德皇帝（明武宗）被写坏是因为接班的嘉靖不是他儿子而是堂兄弟，嘉靖不能把他写太好；明武宗实录是嘉靖指派杨廷和等人编的，有偏颇；正德从江南回来在通州先停半年，先派人打探京城有没有埋伏，说明他很有城府，绝非史料所写那么蠢。
-- **正德与天启轶事**：受访者讲述正德要去江南，大臣跪金水桥前抗议，锦衣卫打死十几个；到扬州要东西不给，让人准备酒席又说吃不了，把酒席折合银两带回去，皇帝打秋风；另一受访者补充天启皇帝爱当木匠，干完活拆大盆去卖，卖完还打听卖得怎么样，成就感特大。
-- **明式家具地位**：受访者认为天启当木匠从侧面反映当时社会时尚，家具在每个人心里地位高，明式家具在国际上地位高绝非偶然，"所有的偶然中一定有个必然的因素"。
-- **明清审美差异**：受访者认为宋明是典型汉人政权、文人政权，文人审美较高，对美的判断不是表象的；满族是异族，进来后对美的判断都是表象的——今天凡是外在直观能看到的都卖得贵，而晚清到民国初年值钱的一定是素雅的。
+- **受访者写明史的原因**：明史资料最多、最熟；历史研究有两个难点，一是先秦（如孙武事迹在史记中仅一两篇且多为编造），二是明清——明实录几千万字、明通鉴、明纪事本末、明会典等堆得比山还高，但一个事件可能有七个不同说法，如同罗生门。
+- **受访者推崇朱元璋**：朱元璋是历史上唯一由最底层乞丐当上皇帝的人，刘邦好歹算村长或乡长；他因要过饭知道每一层的猫腻，疑心重是肯定的；明朝规章制度基本由他定下来，没有太大改动。
+- **受访者认为人的因素最大**：改变时势一定是出现一个人，这是英雄史观；朱元璋天分相当高，如同《亮剑》中的李云龙没上过军事院校却能打仗，是战场上死死生生积累的经验。
+- **受访者谈朱元璋参加起义**：朱元璋在庙里犹豫不去，因信差送信被人听到告发，没办法只能去起义；历史最重要的是明白它是发生过的，旁观者觉得好玩，但当事人是掉脑袋的风险。
+- **受访者谈明末市民生活**：明末很多真相被掩盖，市民生活特别轻松，想去哪去哪，连皇册都不用了；江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍这类市民小说出现是娱乐产品，说明有养活自己的资本。
+- **受访者谈明末艺术**：明末工艺品彻底改观、变得非常精细，日本派大量工匠来交流学习；吴门画派文徵明、唐寅画小桥流水、风雨归舟图，充满欣赏感觉，生活不好画不出那些东西；到八大山人朱耷时画翻白眼，是对社会愤愤不平。
+- **受访者谈历史教训**：我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训；历史事件发生时有背景，你不比前人聪明甚至可能比前人笨，那种情况出现时你也得这么办。
+- **受访者比喻史书与生活**：史书记载下来的是照片，而古人的生活是录像；你不知道那一幕之前和之后是什么，所以不能套用历史经验。
+- **受访者谈明朝灭亡**：1644年明朝首都北京爆发疙瘩瘟（受访者认为可能为天花），李自成打到京城无人抵抗；吴三桂入关理由是为崇祯皇帝复仇，他认为崇祯可以早点跑但不跑。
+- **受访者谈王朝300年大限**：中国历史王朝300年都是大限，逼近300年自己就没了，和人到八九十岁大限快到了一样；严格讲超过300年的只有宋朝，汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
+## 明朝皇帝评价与历史观
+- **受访者认为正德皇帝被写坏**：明武宗实录是嘉靖指派杨廷和等人编的，因嘉靖是堂兄弟接班、拐了个弯，不能把正德写得太好；正德从江南回来没进京城，在通州先停半年派人打探京城有没有人搞埋伏，显示非常有城府。
+- **受访者谈正德皇帝荒淫评价**：正德被定为明朝最荒淫的皇帝，但豹房其实是动物园、养了豹子，后宫也是女人，放哪都一样；他有没有生育能力不好说，但没有正宗传下来，到嘉靖是拐弯。
+- **受访者谈天启皇帝当木匠**：天启皇帝爱当木匠，干完活拆大盆去卖，卖完还打听卖得怎么样，说卖得很好就特有成就感；这从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然。
+- **受访者谈明朝皇帝受制约**：明朝皇帝并非想干什么就干什么，明武宗要去江南，大臣跪在金水桥前抗议，皇帝气坏了到锦衣卫打死了十几个人；到扬州要东西，有也不给，皇帝只好回去，还让人把酒席折合成银两带回去。
+- **受访者谈史官冒死求名**：明朝有些史官把冒死进谏当时尚，就是要跟皇帝说难听的、让皇帝砍头，这样青史留名；受访者认为这是文化的力量，超出我们想象。
+- **受访者谈明末审美差异**：宋明是典型的汉人文人政权，文人欣赏的审美比较高，对美的判断不是表象的；满族是异族，进来后对美的判断都是表象的，所以故宫金碧辉煌的大红大紫是满族趣味；100年前晚清到民国初年值钱的一定是素雅的，今天外在直观能看到的都卖得非常贵。
 # 关键引语与金句
 &gt; “慢慢来才是最快的方法。”
-- 当年明月在讨论日本文化中“不夹杂私心、按自己本分做事”时引述他人观点，用以说明不偷奸耍滑反而更有效率。
+- 背景：当年明月谈日本文化中不夹杂私心、按各自本分做事的生活方式时，引述他人观点说明走捷径是错的。
 &gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
-- 当年明月回应主持人关于明朝兴亡经验教训的提问，指出历史事件有特定背景，不能简单套用经验。
-&gt; “你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办。”
-- 当年明月解释为何不能从历史中轻易吸取教训，强调后人常误以为前人愚蠢，实则身处同样情境未必做得更好。
-&gt; “史书上记载下来的是什么？照片。而我们实际上生活、古人的生活都是录像。”
-- 当年明月说明史书只记录瞬间而缺乏前因后果，导致人们对历史产生误解。
-&gt; “一个人到战场上死死生生多少年，没死，最后积累下来经验……我一上战场我就知道，敌人会往哪走，我该怎么打。”
-- 当年明月以《亮剑》中李云龙为例，说明朱元璋这类人物靠实战经验而非书本知识成就事业。
-&gt; “日本的精神就恰恰相反，他坚持一个原则……当他忘记所有的事情，只记得把这一炮开出去，他就达到了他的最高境界。”
-- 当年明月对比中日文化精神，说明日本文化追求极致、专注单一目标。
-&gt; “中国的文化精神是中庸……不是对也不是错，不是黑也不是白……而是一条最适合的路。”
-- 当年明月以马先生家具店中“硬木刻云彩”为例，阐释中国文化的中庸与融合精神。
-&gt; “日本战后用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然……他是世界上这个强国里唯一没有资源的国家。”
-- 当年明月在讨论日本民族极端精神时，以战后经济崛起为例论证其必然性。</t>
+- 背景：当年明月回应主持人关于明朝兴亡经验教训的提问，指出历史事件发生时有背景，不能简单套用经验。
+&gt; “历史最重要的是什么？就是你要明白它是发生过的……你要明白这事是真的。”
+- 背景：当年明月谈朱元璋被逼上梁山参加起义军一事，强调后人看历史不能只当故事好玩，要意识到那是真实发生过的、有风险的事。
+&gt; “你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。”
+- 背景：当年明月回应主持人关于朱元璋选择是否“逼上梁山”的讨论，说明后人回看历史人物时容易觉得对方不聪明，但当时身处其中看不到全貌。
+&gt; “所有的偶然中一定有个必然的因素。”
+- 背景：马未都谈天启皇帝爱当木匠、明式家具在国际上地位高并非偶然，反映当时社会对家具的重视程度。
+&gt; “日本的文化跟中国的文化存在一个极大的不同……中国的文化精神是中庸。”
+- 背景：当年明月对比中日文化差异，以马未都家具店中硬木刻云彩的家具为例，说明中国讲究融合、不走极端的中庸之道。
+&gt; “日本人的跳槽率是最高的……每一次跳槽都是社会资源的浪费。”
+- 背景：马未都谈日本成为世界经济强国背后被忽略的指标，回应主持人关于日本忠诚文化的讨论。
+&gt; “他不管做到什么机关，甚至被伤害的对方都认为他是出于公心，这很难得。”
+- 背景：马未都谈《大奥》中阿福25岁进大奥当奶妈、65岁去世、40年无私心的忠诚文化具体体现。</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>56</v>
+        <v>61.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17496/3875</t>
+          <t>17496/3662</t>
         </is>
       </c>
     </row>
@@ -13725,68 +13760,65 @@
       <c r="C37" t="inlineStr">
         <is>
           <t># 访谈概述
-余华接受访谈，回顾其写作生涯与创作理念。余华是中国当代作家，代表作包括《活着》《兄弟》《第七天》《文城》等。访谈围绕其写作生涯的1.0/2.0/3.0阶段、《兄弟》的创作与批评、对批评的态度与自我调节、中年危机、未来写作计划、对马尔克斯的反思、网络热度及人生感悟等话题展开。余华最核心的观点包括：其一，写作3.0版本（受威廉·福克纳影响，用视觉描写代替心理描写）以后就没再升级，因为写作已成熟；其二，他认为自己40多岁到50岁最好的写作时间浪费了，只出了两部作品，剩下的写作时间可能只有十年左右；其三，他不再追求高度，而是追求宽度，但也不排除最后一部作品创造新高度的可能性。访谈锚点包括《兄弟》（1996年开始创作，2003-2004年重写）、《第七天》及三亚。看点在于余华亲述童年被海流带走的经历，以及他澄清莫言在莎士比亚故居发誓要成为剧作家是「瞎扯」，并透露互联网上关于他说的话有一半不是他说的。
+本次访谈中，作家余华（代表作《活着》《兄弟》《第七天》《文城》）接受采访，回顾其写作生涯的1.0/2.0/3.0阶段划分，分享《兄弟》出版遭遇批评的经历、对批评的态度与自我调节方式，并谈及中年危机、互联网热度下的公众人物身份及未来写作计划。访谈主线覆盖写作阶段、作品批评、中年危机、文学理想、网络热度与人生姿态等议题。余华最核心的观点包括：写作3.0版本（视觉描写代替心理描写）已足够，如《活着》虽可能被视为4.0版但已不是难题；对待批评第一不要看、第二要重视有道理的批评；对高度已不追求，现在追求宽度。访谈锚点包括《兄弟》创作始于1996年、2004年重写，以及《第七天》出版时只接受一个采访。看点在于余华亲述少年时在杭州湾被海流带至40里外、靠仰泳看天空判断方向最终获救的经历，以及他明确指出互联网上关于他说的话有一半不是他说的。
 # 访谈详细记录
 ## 写作生涯的1.0/2.0/3.0阶段
-- **1.0阶段**：余华认为文学创作第一个重要时刻是逼自己坐下来写，让屁股和椅子建立友谊；他回忆若没有离开写字桌躺到床上幻想作品多么厉害，可能就不会去写它。
-- **2.0阶段**：受卡夫卡启发，写作越写越难，遇到心理表现的障碍；余华认为若写人物内心平静没有意思，内心动荡不安则写1万字也不够。
-- **3.0阶段**：受威廉·福克纳影响，采用视觉描写代替心理描写——让心脏停止跳动、让眼睛睁开；他举例《狂人日记》中"赵家的狗看了我一眼"，一下就知道人物精神状态。
-- **3.0以后未再升级**：余华认为3.0版本以后就没再升级，因为写作已成熟；《活着》虽可能被视为4.0版，但对他已不是难题，知道写没文化的农民必须用最朴素的语言。
+- **1.0版本**：余华认为文学创作第一个重要时刻是逼自己坐下来写，让屁股和椅子建立友谊；假如不坐下来写，躺在床上幻想作品成功没有用。
+- **年轻时的目标**：余华当时的目标是对着托尔斯泰和陀思妥耶夫斯基去的，现在知道距离不可逾越；这种野心支撑他一篇篇写下来，同时对自己的写作不满意。
+- **2.0版本**：受卡夫卡启发，写作越写越难，遇到心理表现障碍；写一个人物内心平静没有意思，内心动荡不安可以写1万字。
+- **3.0版本**：受威廉·福克纳启发，采用视觉描写代替心理描写——让心脏停止跳动、让眼睛睁开；如《狂人日记》中「赵家的狗看了我一眼」，一下就知道人物精神状态。
+- **3.0之后**：余华认为3.0版本以后就没再升级，因为写作已成熟；《活着》可能被视为4.0版，但对他来说已不是难题，知道写农民要用最朴素的语言。
 ## 《兄弟》的创作与批评
-- **创作时间线**：《兄弟》创作始于1996年，因当时中国社会变化复杂而写；2003年和2004年重新拿回来写时，庆幸1996年没有写完，因为从2004年再看，96年时候的变化不算什么，那才是真正大的变化。
-- **出版期待与落差**：余华说《兄弟》出版时认为肯定是一片赞扬，带着这样的期待去，结果一片骂声，弄得他有点糊涂；当时互联网已形成浪涛，他努力想把骂声引过来，接受了很多采访去解释作品。
-- **《第七天》与《文城》的反响**：到《第七天》出来时余华只接受了一个采访，什么都不做让他们去骂；他提前告诉朋友们要做好思想准备，结果果然一片骂声；《文城》出来时骂声还有但少一点，他调侃"骂人的人也累"。
+- **创作时间线**：《兄弟》创作始于1996年，2003年和2004年（尤其2004年）重新拿回来写；余华庆幸1996年没有写完，因为2004年再看，96年时候的变化不算什么，那才是真正大的变化。
+- **出版期待与落差**：余华说《兄弟》出版时认为肯定是一片赞扬，带着这种期待去，结果一片骂声；当时互联网已存在，批评形成浪涛，他努力想把骂声引过来，接受了很多采访去解释作品。
+- **批评应对**：到《第七天》出来时只接受了一个采访，什么都不做让他们骂；《文城》出来前提醒朋友做好准备，骂声有但少一点，骂人的人也累了。
 ## 对批评的态度与自我调节
-- **对待批评的方式**：余华认为第一就是不要去看，第二有些批评要重视；有些批评没有道理，比如批评宋凡平人物太完美——宋凡平是阶段性出现的人物，只能写他在这个阶段的表现，没有一个从头到尾贯穿的人物才需要写得丰富。
-- **有道理的批评**：余华认为"社会底层人也未必都那么善良"这句关于《第七天》的批评说得很好；他解释《第七天》必须把善良在死无葬身之地表现出来，否则没有力量，但写现实生活中的勾心斗角不能太邪恶，这种考虑会在以后写小人物时纳入。
-- **互联网上的误传**：余华说互联网上关于他说的话有一半不是他说的，比如"想要命好的"、"精神内耗就是心里的戏太多"都不是他说的。
+- **对待批评的方式**：余华认为第一不要去看，第二有些批评要重视；有些批评没有道理，有些批评可以提醒后面的作品。
+- **批评宋凡平太完美**：余华认为这种批评没有道理，因为宋凡平不是李光头和宋刚那样贯穿全书的人物，只是阶段性出现的人物，只能写他在这个阶段的表现。
+- **批评《第七天》底层人未必都善良**：余华认为这句话说得很好，会在以后写小人物的作品中考虑进去；《第七天》是特殊情况，必须把善良在死无葬身之地表现出来，但写现实生活时他们也会勾心斗角，只是不会置对方于死地。
 ## 中年危机与自我调节
-- **34岁时的感受**：余华在年终总结中写道，一个成年人每到年底都会发现一种虚无；当时感觉生活每天都在呼吸，但人口增加了、孩子来了，空间并没有因此变得宽敞一点。
-- **中年危机的本质**：余华认为突然发现没有那么多新的东西，只有写作能够得到一些新的东西，虚构的世界带来新东西，而现实世界每天重复；这是所有人都会遇到的中年危机。
-- **自我调节方法**：余华建议面对负面消息太多时可以选择屏蔽不看，因为发生的事情我们无法选择什么让它发生，但可以选择什么让自己知道、什么让自己不知道；哪怕知道可能是真的，也可以选择不看。
-## 未来写作计划与对高度和宽度的追求
-- **浪费的时间与剩余时间**：余华认为自己40多岁到50岁最好的一段时间浪费掉了，只出了两部作品；他估计能够好好写作的时间可能还有十年左右。
-- **未完成的长篇小说**：余华提到2006年开始写的一部长篇小说，时间跨度跟《兄弟》一样，但从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式去写；现在身体状态可能还能维持这种激烈，但那个感觉没了，80年代和90年代的感觉都在远去，很难找回来。
-- **写作计划**：余华计划先写完一个喜剧，想改变读者对他的印象，让读者不再觉得这个人那么悲观；他提到开学时去和学生见面，处理学校事务后回到三亚继续写作，安安静静把感觉找回来。
-- **从追求高度转向宽度**：余华表示对高度已经不追求了，现在追求宽度；他认为作为作家能走到的高度就是现在的高度，允许自己下滑一下但不要下滑太多，年纪大了知道自己的能力在哪里、还有多少潜力；但也不排除运气来了在最后一部作品上创造新高度的可能性。
-## 对马尔克斯的反思与文学理想
-- **被马尔克斯误导的一代**：余华认为他们这一代中国作家在很大程度上都被马尔克斯误导，整整一代都想在一本书里写一个世纪的故事，但其实没有必要；托尔斯泰、狄更斯、莎士比亚、巴尔扎克、福楼拜、司汤达、契诃夫都是写自己时代的故事。
-- **对马尔克斯的补充看法**：余华认为马尔克斯开创了一个先例，但没有能力在一个不到30万字的小说里面写出一个世界；马尔克斯所写的拉丁美洲世界是最混乱的世界，所以他能够写出来，不是别人都写得出来。
-- **莫言在莎士比亚故居发誓是瞎扯**：余华澄清莫言在莎士比亚故居发誓要成为剧作家是瞎扯；莫言小说对话很精彩，20多年前就开始写话剧了，只是写了没拿出来；余华与苏童、莫言三人一起去莎士比亚故居，莫言在挑选帽子，帽子钱还是余华付的，买了三顶一模一样的深蓝色帽子，上面有莎士比亚名字，后来找不着了。
-## 对网络热度的看法
-- **走红后的冷静期**：余华因互联网走红后停了一年，任何活动、任何采访都不做；当时有节目联系他，他说抱歉，现在在一年的冷静期中间，因为按照过去的经验，只要一年在媒体上消失就马上过去了。
-- **自媒体时代的不同**：余华发现自媒体时代不是这样，会把几十年前的事情都翻出来，以前说过的话也给你翻出来；互联网上关于他说的话有一半不是他说的。
-- **不担心喜欢会消散**：余华不担心网红热度会消散，因为他的工作不是说话，是写作；可能今天因为一句话突然被人关注，又说错一句引发愤怒，过了十年以后又众人喜欢，但对他来说不说话也挺好。
+- **34岁的年终总结**：余华34岁时年终总结发现一种虚无，感觉生活每天都在呼吸，但人口增加了、孩子来了，空间并没有因此变得宽敞一点。
+- **中年危机的本质**：余华认为这是所有人都会遇到的中年危机，现实世界每天重复，只有写作能够得到一些新的东西，虚构的世界带来新东西。
+- **自我调节方法**：余华认为发生的事情我们无法选择什么让它发生，但可以选择什么让自己知道、什么让自己不知道；网上负面消息太多时就不看，屏蔽掉，我们有这个权利和能力选择积极的。
+## 未来写作计划与文学理想
+- **下一步计划**：余华希望下一步作品快一点，开学时去和学生见面，处理学校事务后回三亚继续写作，安安静静把感觉找回来。
+- **对高度与宽度的追求**：余华表示对高度已经不追求了，现在追求宽度；作为作家，写作能走到的高度就是现在的高度，允许自己下滑一下但不要下滑太多。
+- **被马尔克斯误导**：余华认为我们这一代作家在很大程度上被马尔克斯误导，整整一代中国作家都想在一本书里写一个世纪的故事，但没有能力在不到30万字的小说里写出一个世界。
+- **写作方向**：余华现在知道要什么，把所处时代通过更多方式表现出来；运气来了可能在最后一部作品上创造新高度，但不去想。
+## 互联网热度与公众人物身份
+- **网络言论失真**：余华说在互联网上看到的关于自己说的话，有一半不是自己说的；如「想要命好的」「精神内耗，心里的戏太多」都不是他说的。
+- **冷静期经历**：余华曾停了一年，不做任何活动和采访；按照过去经验，一年不在媒体上出现就会消失，但自媒体时代会把几十年前的事情翻出来。
+- **对热度消散的态度**：余华不担心喜欢会消散，因为工作不是说话而是写作，不说话其实也挺好。
 ## 人生感悟与姿态
-- **第一次看到大海的感受**：余华童年第一次看到大海时，没有看到过如此宽阔辽阔的景象，感觉到一种宽阔的感觉，所以领悟到人生就是宽广的；小时候的人生感受是向前看的，现在是往后看的，回忆占多了。
-- **海流中游泳的经历**：余华讲述小时候每年夏天在海盐游泳，有一天发现自己进入海流，知道不能挣扎只能跟着走，一直到了40里外的平湖乍浦才爬上来，赤脚沿着海边走回来，天快亮了；刚开始紧张害怕以为要死在海里，后来放心，最后被海流带回家，那一刻真的感动了，觉得海浪带我回家了。
-- **三亚的星空与月光**：余华说在三亚看到了小时候的天空，因为这地方没有污染；晚上经常和太太走路看天空看月亮，月亮经常出现光晕，通过光晕发现月光是金色的，不是银色的。
-- **希望留下的姿态**：余华希望在历史长河中留下的姿态是遗忘的姿态；那些能够勉强被微风吹进耳朵的人，那也是勉强吹进来的，假如历史的长河里有一个主题，这个主题就是一个一个世界、一个一个的人。
+- **希望以遗忘的姿态存在**：余华希望以遗忘的姿态留在历史长河，那些能够勉强被微风吹进耳朵的人也是勉强吹进来的。
+- **历史长河的主题**：余华认为假如历史的长河里有一个主题，这个主题就是一个世界、一个一个的人。
+- **童年游泳经历**：余华小时候每年夏天在海盐游泳，有一天进入海流，知道不能挣扎只能跟着走，一直到了40里外的地方才爬上来，赤脚沿着海边走回来，天快亮了。
+- **对海流的感受**：余华说海流对很多人来说可能是坏事，但那一刻对他来说，如果没有遇到海流，可能就回不来了；海流只会把他带回家，带回海岸线。
 # 关键引语与金句
 &gt; “假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的，坐下来让屁股和椅子建立友谊，这是很重要的。”
-- 回应文学创作1.0阶段最重要的时刻是什么。
+- 背景：回应主持人关于文学创作1.0阶段的提问，谈年轻时写作的第一个重要时刻。
 &gt; “当时我觉得我将可能我的目标是对着那个托尔斯泰和陀思妥耶夫斯基去的，现在我知道我离他们的距离是不可逾越的。”
-- 谈到年轻时写作的野心与幻想。
+- 背景：回应主持人问当时觉得最厉害能去到什么，谈年轻时写作的野心与幻想。
+&gt; “福克纳所采用的方式就是让心脏停止跳动，让眼睛睁开。心理描写没有心理，它是视觉描写。”
+- 背景：谈3.0版本受威廉·福克纳启发，用视觉描写解决心理描写难题。
+&gt; “兄弟出版的时候，我认为肯定是一片赞扬，我是带着这样的一种期待去的，结果一片骂声弄得我有点糊涂。”
+- 背景：回应主持人关于《兄弟》出版时面对批评的提问，谈当时对作品反响的预期与落差。
 &gt; “我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。”
-- 谈到2006年开始写的一部长篇小说因感觉远去而搁置，感慨浪费了最好的写作时间。
-&gt; “把悲伤留给虚构，把欢乐留给现实。”
-- 谈到自己作品几乎都是悲剧，想先写完一个喜剧改变读者印象。
-&gt; “我能够走到的高度已经就是我现在的高度，我能够允许自己下滑一下，但再不要下滑得太多。”
-- 谈到不再追求高度，转而追求宽度。
-&gt; “我们整整一代中国作家都想在一本书里边写那个一个世纪的故事，但是其实没有必要。”
-- 谈到马尔克斯对一代中国作家的影响与反思。
-&gt; “现在在互联网上，起码我看到的我看到的啊，关于我的说的话，有一半不是我说的。”
-- 谈到自媒体时代被翻出旧事、被安上非本人说过的话。
-&gt; “假如那个历史的长河里边有一个主题的话，这个主题就是遗忘的姿态。”
-- 回应希望以什么样的姿态留在历史长河中。</t>
+- 背景：谈2006年开始写的长篇小说未完成，感慨当年感觉远去、最好写作时间被浪费。
+&gt; “发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。”
+- 背景：回应主持人问年轻人如何排解不安与焦虑，谈自我调节的方法。
+&gt; “现在在互联网上，起码我看到的，关于我说的话，有一半不是我说的。”
+- 背景：回应主持人谈互联网热度与公众人物身份，指出网上流传的许多话并非自己所说。
+&gt; “遗忘的姿态。就是一个遗忘的人。”
+- 背景：回应主持人问希望以什么样的姿态留在历史长河。</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>70.8</v>
+        <v>57.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11212/3761</t>
+          <t>11212/3048</t>
         </is>
       </c>
     </row>
@@ -13897,79 +13929,81 @@
       <c r="C38" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讲座为访谈式讲解，主讲人围绕柏林战役展开介绍，涵盖战役背景、双方兵力部署、战役过程、结局及影响，并解答听众关于城市作战、希特勒自杀、英美未攻柏林、影视书籍推荐等问题。战役背景方面，1945年苏军进抵奥德河-尼斯河一线，距柏林60公里；英美联军在易北河，距柏林100-120公里。苏军参战部队为白俄罗斯第一方面军（朱可夫元帅）和乌克兰第一方面军（科涅夫元帅），总计约250万人；德军防守部队包括中央集团军群残部、柏林卫戍部队及国民掷弹兵部队，总兵力约100万人。战役过程：1945年4月16日苏军炮轰德军阵地并越过奥德河、尼斯河；4月20日左右进抵柏林城区（潘科区及帕卡洛镇），4月24日突进市区；4月30日希特勒与妻子爱娃·布劳恩在地堡自杀，尸体被部下焚烧；4月30日夜间苏军占领国会大厦；5月2日柏林德军全部投降，战役结束；5月9日德国宣布无条件投降，二战欧洲部分正式结束。战役影响：奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直至1990年统一；日本于1945年9月2日在密苏里号军舰上签署无条件投降书，二战彻底结束。
+本次讲座由主讲人（原文未提及姓名）以采访/对话形式讲解柏林战役，面向对二战史感兴趣的听众。讲座围绕战役背景与双方态势、兵力部署、战役进程与关键事件、城市作战特点、英美未攻柏林原因、战役细节与影视推荐、战役影响与后续历史等板块展开。核心判断包括：柏林战役是二战欧洲战场最后一次大规模战斗，也是人类历史上最大规模的城市作战；苏军以约250万人对德军约100万人形成合围，从什切青到德累斯顿实施合围；战役奠定冷战欧洲部分基调，德国分裂为东西两个德国直至1990年统一。关键锚点：苏军距柏林60公里、英美联军距柏林100—120公里；1945年4月16日开战、5月2日结束、5月9日德国无条件投降。对听众而言，讲座提供了战役全貌及希特勒自杀、红旗插上国会大厦等标志性细节，并推荐了苏联《柏林战役》与德国《帝国的毁灭》两部影视作品。
 # 核心观点与论证
-## 战役背景与战略态势
-- **战役定位**：柏林战役是第二次世界大战欧洲战场的最后一次大规模战斗，也是苏德战争期间苏联和德国进行的最后一场大规模战役。
-- **苏军先机**：1945年苏军已进抵奥德河、尼斯河一线（今德国和波兰边境地区），距离柏林仅60公里；英美联军才到达易北河一带，距离柏林100–120公里，苏联获得先发制人机会。
-- **苏军部署**：白俄罗斯第一方面军（指挥官朱可夫元帅）从奥德河—法兰克福方向北部对柏林突击与包围；乌克兰第一方面军（指挥官科涅夫元帅）由克拉科夫及德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。
-- **德军兵力**：防守部队为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（由年纪较大的老人和16岁以下孩子组成的民兵），总兵力约100万人，从柏林到桑多梅日桥头堡及奥德河一带布防。
-- **苏军兵力**：白俄罗斯第一方面军和乌克兰第一方面军总计约250万人，从北部什切青到南部德累斯顿形成合围网。
+## 战役背景与先发优势
+- **战略意义**：柏林战役是第二次世界大战欧洲战场最后一次大规模战斗，也是苏德战争期间苏联和德国进行的最后一场大规模战役；1945年同盟国和苏俄已从不同方向攻入德国本土，纳粹政权覆灭只是时间问题。
+- **苏军位置**：苏军进抵奥德河、尼斯河一线（今德国和波兰边境地区），距离柏林仅60公里；英美联军才到达易北河一带，距离柏林还有100–120公里，苏联已获得先发制人机会。
+- **占领动机**：苏联从上到下团结一致，以柏林为目标进行不惜代价的强攻——占领柏林可获得至高无上荣誉，因柏林是法西斯德国大本营及纳粹最大巢穴，谁占领柏林谁就在二战后获得至高无上地位。
+## 双方兵力与合围部署
+- **苏军部署**：白俄罗斯第一方面军（指挥官朱可夫元帅）从奥德河一线、奥德法兰克福方向北部对柏林突击与包围；乌克兰第一方面军（指挥官科涅夫元帅）由克拉科夫及德雷斯顿方向前出，从南部绕至波斯坦地区实施西部包围。
+- **德军构成**：防守部队主要为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（由年纪较大的老人和16岁以下孩子组成的民兵），总兵力约100万人，从柏林到桑多梅日桥头堡及奥德河一带布防。
+- **兵力对比**：苏军两个方面军总计约250万人，从北部什切青到南部德累斯顿形成合围网，对柏林实施合围。
 ## 战役进程与关键节点
-- **第一阶段**：1945年4月16日，苏军以数以千计的火炮和卡秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击。
-- **推进受阻**：因德军在桑多梅日桥头堡修筑防线，苏军拖至4月20日左右才进抵柏林城区（今柏林潘科区及帕卡洛镇一带），4月24日白俄罗斯第一方面军突进柏林市区，科涅夫部队仍在向柏林边缘靠近。
-- **德军抵抗**：德军温克第十二集团军与苏军一直周旋，是战役中表现突出的部队之一。
-- **希特勒之死**：4月29日希特勒与情妇爱娃·布劳恩举行婚礼；4月30日，柏林已被苏军围死、苏军距其地堡仅两条街，希特勒不甘被俘，与爱娃·布劳恩一起饮弹自尽。
-- **战役结束**：4月30日夜间苏军占领德国国会大厦；5月2日经谈判拉扯，柏林城防司令魏德林宣布柏林其余地区德军向苏军缴械投降，柏林战役结束；5月9日德国宣布无条件投降，二战欧洲部分正式结束。
-## 城市作战特点
-- **定义与危险**：城市作战中敌人可能从任何方向攻击，坦克和车辆在街道上易受攻击，敌人可从建筑物或其他街道用火箭筒和机枪攻击，非常困难且危险。
+- **第一阶段突击**：1945年4月16日，苏军以数以千计的火炮和卡秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击；因德军在桑多梅日桥头堡的防线修筑，苏军拖至4月20日左右才进抵柏林城区（今柏林潘科区及帕卡洛镇一带）。
+- **突入市区**：4月24日白俄罗斯第一方面军突进柏林市区，科涅夫元帅的乌克兰第一方面军仍在艰难摸索向柏林边缘靠近；德军温克第十二集团军与苏军一直周旋。
+- **希特勒之死**：4月29日希特勒与爱娃·布劳恩举行婚礼；4月30日柏林已被苏军围死、红军离地堡仅两条街距离，希特勒不甘兵败被俘，与夫人举枪自尽，部下用汽油焚烧其尸体，至今未见遗体全貌，仅获烧焦焦炭。
+- **战役结束**：4月30日夜间苏军占领德国国会大厦；5月2日苏德双方谈判拉扯后，柏林德军全部缴械投降，城防司令魏德林宣布柏林其余地区德军向苏军投降，柏林战役结束；5月9日德国宣布无条件投降，将所属领空、领海、机械设备及仍控制的海外属地（荷兰、丹麦、挪威、波罗的海三国地区、捷克斯洛伐克）交与英美盟军及苏俄最高统帅，二战欧洲部分正式结束。
+## 城市作战的危险特性
+- **作战定义**：城市作战中敌人可从任何地方攻击（`具体内容`：敌人可能从建筑或街道以火箭筒和机枪攻击街道上的坦克和车辆），对进攻方非常困难和危险。
+- **战场差异**：城市街道限制坦克和车辆机动，敌方利用建筑掩护从四面八方发起攻击，与野外作战的正面交锋有明显区别。
 ## 英美未攻柏林的原因
-- **战后协议**：盟国事先已就战后德国地盘划分达成协议，柏林战后属于苏联，但会分出一半区域给西方盟国（即后来的西柏林）。
-- **艾森豪威尔考量**：美军统帅艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后仍需撤出，得不偿失。
-- **战略取舍**：西方盟军更倾向占领德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等；且打完德国后盟军还有求于苏联协助对日作战。
-## 战役细节与影响
-- **易北河会师**：西欧部队与东边苏联部队事先没有交流，在易北河会师只是偶然，双方见到对方部队才知道合拢，高层未达成共识。
-- **红旗插国会大厦**：著名的「红旗插上国会大厦」照片中，红旗并非标准苏军制式军旗，而是士兵临时用床单和颜料绘制；插旗士兵手上戴有三块从德国老百姓抢来的手表，摄影师为国际观瞻要求重新摆拍。
-- **战后格局**：柏林战役奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直至1990年两个德国才统一。
-- **二战终结**：日本于1945年9月2日在密苏里号军舰上签署无条件投降书，第二次世界大战彻底结束。
+- **战后协议**：盟国事先已在战后德国地盘划分上达成协议，柏林战后属于苏联，柏林会分出一半区域给西方盟国（即后来的西柏林）。
+- **艾森豪威尔考量**：美军统帅艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤出（整个德国东部都是苏联占领区），得不偿失；与其如此，不如尽可能占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等德国精华地带。
+- **对日作战需求**：打完德国后盟军还有求于苏联，需要苏联帮助一起对日本作战；丘吉尔虽想抢占柏林，但受上述协议与考量制约。
+## 战役细节与史实补充
+- **易北河会师**：西欧部队与东边苏联部队事先没有交流，双方在易北河会师只是偶然，见到对方部队才知道合拢，事先双方高层未达成共识，各打各的。
+- **红旗插国会大厦**：著名历史照片「红旗插上国会大厦」中的红旗并非标准苏联制式军旗，而是士兵临时用床单和颜料绘制；插旗士兵手上戴有三块从德国老百姓手里抢来的手表，摄影师认为有碍国际观瞻，让其重新摆拍、不把手表明面戴在手上。
+- **残余部队去向**：第九集团军及温克第十二集团军残余部队在温克率领下渡过易北河，向英美盟军投降。
+## 战役影响与后续格局
+- **冷战基调**：柏林战役奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿今天的罗斯托克到南部图林根一线形成，此后一直持续到1990年两个德国才统一。
+- **二战终结**：日本于1945年9月2日在密苏里号军舰上签署无条件投降书，代表第二次世界大战彻底结束。
 # 金句总结
-&gt; 谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。
-- 背景：讲到柏林战役对苏联的战略意义时，强调占领柏林在战后国际格局中的象征性价值。
-&gt; 此时对于纳粹德国来说可以说是丧钟敲响的开始。
-- 背景：讲到苏军已进抵奥德河—尼斯河一线、距柏林仅60公里时，对德军处境的判断。
-&gt; 城市作战……敌人可能从任何方向攻击，坦克和车辆在街道上易受攻击，非常危险。
-- 背景：回答主持人关于城市作战与野外作战区别的提问时，用英文简要描述城市作战的危险性。
-&gt; 希特勒不甘于在兵败之后被苏联俘虏，所以说他举枪自尽了。
-- 背景：回答听众关于希特勒是否自杀的提问时，说明其自杀动机。
-&gt; 大部分人都坚信纳粹没有覆灭，还在就是以自欺欺人的方式麻痹自己和苏军进行的就是不同程度的战斗。
-- 背景：解释希特勒尸体被焚烧、遗体下落不明导致外界谣言盛行时，指出当时德军内部的自欺欺人心态。
-&gt; 与其这样，还不如说是尽可能去占领更多德国的精华地带……柏林就让给苏联吧。
-- 背景：回答英美为何不攻打柏林时，转述艾森豪威尔的战略考量——占领柏林得不偿失，不如占领慕尼黑、斯图加特等德国精华地带。
-&gt; 那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜。
-- 背景：补充听众提到的易北河会师细节时，说明红旗插上国会大厦著名照片中旗帜的临时制作背景。
-&gt; 奠定了冷战欧洲部分的一个基调。
-- 背景：回答柏林战役胜利后的世界格局时，指出战役对德国分裂为东西两个德国、冷战欧洲格局形成的深远影响。
+&gt; “谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。”
+- 背景：讲到苏联从高层到基层团结一致、不惜代价强攻柏林的原因。
+&gt; “城市作战……敌人可以从任何地方攻击你的部队，你的坦克和车辆就在街上，敌人可能从建筑或街道用火箭筒和机枪攻击你，这非常困难和危险。”
+- 背景：回答主持人关于城市作战与野外作战区别的提问。
+&gt; “因为在他自尽之后，他的部下用汽油把他的尸体给焚烧了。然后到今天为止，也没有见到希特勒遗体的全貌，只是获得一堆已经被烧焦的焦炭。”
+- 背景：解释希特勒自杀细节争议的由来。
+&gt; “大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗。”
+- 背景：说明希特勒尸体被焚后民间谣言盛起的原因。
+&gt; “你占领了柏林，你还是要只是把西柏林占在自己的手里，但是整个德国东部都是苏联的占领区，意味着西方盟军还要撤回去，所以说得不偿失。”
+- 背景：解释英美为何不攻占柏林，艾森豪威尔的考量。
+&gt; “与其这样，还不如说是尽可能去占领更多德国的精华地带，比如说慕尼黑、斯图加特以及纽伦堡、汉堡、法兰克福这些地方的柏林就让给苏联吧。”
+- 背景：承接上句，说明西方盟军选择占领德国精华地带而非柏林。
+&gt; “那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜，但是这个非常具有代表性的意义。”
+- 背景：补充红旗插上国会大厦照片的细节。
+&gt; “那个插旗士兵手上还带着三块从德国老百姓手里抢来的手表，摄影师觉得这个有碍国际观瞻，所以让那个士兵重新摆拍。”
+- 背景：补充著名照片《红旗插上国会大厦》的摆拍内情。
 # Q&amp;A 环节
-**听众**：城市作战跟野外作战有什么明显区别或定义吗？
-**主讲人**：城市作战中敌人可能从任何方向攻击你，你的坦克和车辆就在街道上，敌人可以从建筑物或其他街道用火箭筒和机枪攻击你的部队，所以非常困难和危险。
+**听众**：城市作战跟野外作战有什么明显区别？有什么定义吗？
+**主讲人**：城市作战中敌人可能从任何地方攻击你，你的坦克和车辆在街道上，敌人可能从建筑或其他街道用火箭筒和机枪攻击，非常困难和危险。
 **听众**：是不是这个战役里面希特勒自杀了？
-**主讲人**：是的。1945年4月30日，柏林已被苏军围死，苏联红军距离希特勒所在的地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，于是举枪自尽，和他的夫人爱娃·布劳恩一起。
+**主讲人**：是的。1945年4月30日，柏林已被苏军围死，苏军距希特勒地堡仅两条街，希特勒不甘被俘，与夫人艾娃·布劳恩一起举枪自尽。
 **听众**：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么受关注？
-**主讲人**：因为他自尽后，部下用汽油把他的尸体焚烧了，到今天为止没有见到他遗体的全貌，只获得一堆烧焦的焦炭，所以外界说法不一，没有确切证据。除了少数亲信外，大部分人坚信纳粹没有覆灭，以自欺欺人的方式麻痹自己继续战斗，各种流传民间的说法褒贬不一，导致谣言盛行。
-**听众**：想更详细了解这个战役，有什么影视推荐吗？有拍成影视吗？
-**主讲人**：苏联有他拍的《柏林战役》，德国有《帝国的毁灭》。
-**听众**：那他们的细节或倾向有什么不同？
-**主讲人**：德国角度更多是希特勒最后生平以及他关于柏林防守的人事任命；苏联方面更多强调从高层到基层的各方面描写，高层的运筹帷幄以及基层官兵的舍生忘死。
-**听众**：主要进攻柏林的是苏联方面的部队吗？
-**主讲人**：是的，同时半数的还有波兰共产党的部队。
+**主讲人**：他自尽后部下用汽油焚烧其尸体，至今未见到遗体全貌，只获得烧焦的焦炭，外界说法不一，没有确切证据。除少数亲信外，大部分人坚信纳粹没有覆灭，以自欺欺人的方式继续战斗，导致民间谣言盛起。
+**听众**：想更详细了解这场战役，有什么影视推荐吗？
+**主讲人**：苏联有《柏林战役》，德国有《帝国的毁灭》。德国角度更多描写希特勒最后生平及柏林防守的人事任命；苏联方面强调从高层到基层的描写，高层运筹帷幄和基层官兵舍生忘死。
+**听众**：主要进攻柏林的是苏联方面的部队？
+**主讲人**：是的，同时还有半数波兰共产党的部队。
 **听众**：那为什么英美不打柏林呢？
-**主讲人**：丘吉尔当时想抢占柏林，但盟国事先已就战后德国地盘划分达成协议，柏林战后属于苏联，会分出一半区域给西方盟国（即后来的西柏林）。美军统帅艾森豪威尔认为攻占柏林会增加不必要伤亡，且占领后还要撤出，得不偿失，不如尽可能占领德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等。而且打完德国后盟军还有求于苏联一起对日作战。
+**主讲人**：丘吉尔曾想抢占柏林，但盟国事先已达成协议，柏林战后属苏联，西方盟国只占西柏林。艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤出，得不偿失；不如占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等精华地带。且打完德国后盟军还有求于苏联共同对日作战。
 **听众**：这场战役大概持续了多久？
 **主讲人**：从4月16日开始，一直进行到5月2日。
 **听众**：有什么书可以看的吗？
-**主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记里关于柏林战役后苏俄和西方博弈的内容，涉及西柏林地区划分和德国边境重新划定。
-**听众**：当时柏林战役胜利之后，世界形成了怎样的格局？
-**主讲人**：奠定了冷战欧洲部分的基调，德国后来分裂成东西两个德国，边界大致沿今天的罗斯托克到南部图林根一带形成，此后一直到1990年两个德国才统一。
-**听众**：B站上比较火的鬼畜片段就是这个战役末期发生的吗？
+**主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记中关于柏林战役后苏俄与西方博弈的部分，涉及西柏林划分和德国边境重新划定。
+**听众**：柏林战役胜利之后，当时世界形成了怎样的格局？
+**主讲人**：奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直到1990年两个德国才统一。
+**听众**：B站上比较火的鬼畜片段就是这场战役末期发生的？
 **主讲人**：对，那个希特勒鬼畜片段出自电影《帝国的毁灭》，尤其是他大骂温克丢下柏林逃跑那一段。</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>49.1</v>
+        <v>55.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4609/3773</t>
+          <t>4609/3973</t>
         </is>
       </c>
     </row>
@@ -14118,58 +14152,69 @@
       <c r="C39" t="inlineStr">
         <is>
           <t># 全文摘要
-会议为多人自由讨论，共5位发言人参与，围绕社会规则合理性、理想工作形态、AI与机器人未来及语音分离标注测试等话题展开。讨论认为必须买房、结婚等规则不合理，工作应基于兴趣而非与金钱挂钩；理想工作形态方面，有观点认为应让AI承担苦活累活，而非从事创作艺术。关于机器人意识与人类未来，存在机器人可能罢工、反抗并奴役人类的担忧，也有观点认为机器人只需执行命令、不必有思想。会议以分享为主，未形成明确结论。
+会议为多人自由讨论，共5位发言人参与，围绕社会约定俗成规则（结婚、买房、工作）的合理性展开，延伸至理想工作形态、AI与机器人承担苦活累活的可能性、机器人拥有思想意识后的风险，以及数码宝贝等作品中的机器人思想构想，最后简短提及语音分离标注测试。讨论中，发言人1认为买房、结婚等规则在经济不好时不可行，工作合理但应做自己想做的；发言人2担忧机器人有思想后可能罢工、反抗并奴役人类，可能成为犯罪代理人或职业杀手，反抗后果灾难性；发言人3认为必须工作是合理的，应让AI做苦活累活而非创作艺术；发言人5认为机器人只需接受命令执行命令，无需思想。以分享为主，未形成明确结论。
 # 分段速览
-## 00:00:02-00:01:40 社会规则合理性讨论
-发言人1提出必须买房、必须结婚等社会规则不合理，经济不好时更不可行；发言人2补充必须结婚生子，并认为结婚、买房、升职都取决于遇到的人和自身经济能力，不能说得太绝对；发言人3认为历史对静辉来说都是合理的，并指出人必须工作是合理的。发言人1进一步表示，人不工作不产生财富世界无法运转，工作本身可能合理，但应做自己想做的事，不应与金钱挂钩。
-## 00:01:40-00:04:13 理想工作形态与AI替代劳动
-发言人2询问大家理想中的工作状态，发言人1表示每天按兴趣干活最好；发言人4提出不干活更好的可能性；发言人3举例宠物博主工作轻松，发宠物视频剪视频即可赚钱，发言人2补充游戏高手也可行。发言人1指出总有些脏活累活没人愿意承担，发言人3认为应让AI做苦活累活而非创作艺术。发言人2引用蔡明小品中机器人反叛情节，讨论机器人替代劳动后人类幸福感是否提升，发言人1认为机器人负责生产、人负责享受虽好但规则难以实现，并提到上层可能不愿让平民过得太好、存在阶级优势。
-## 00:04:13-00:08:05 机器人意识与人类未来
-发言人5提到扫地机器人未来可发展为在家打扫做饭的机器人，发言人1认为以后养老靠自己。发言人2担忧机器人有独立思想意识后可能罢工、反抗并奴役人类，类似《终结者》剧情；发言人3提到斯皮尔伯格人工智能电影也是类似结局，并认为智能和思想可能无法分开；发言人5认为机器人只需接受命令执行命令，不必有思想，但思想可能带来不良影响。发言人2列举军队单兵装甲外骨骼、智能枪械、排雷机械狗等半机械人应用，并引用游戏《重返德军总部》超级战士和数码宝贝中机械邪龙兽等例子。
-## 00:08:05-00:10:56 动漫举例与语音分离测试
-发言人2详细讲述数码宝贝中安多路兽被黑色魔轮控制后仍能通过人脸识别判断身份的情节，认为九几年日本人已有此构想，并提到机械邪龙兽是精密超级计算机形成的生命体；发言人4询问具体出处，发言人2确认是第一二部内容。发言人3提醒时间，随后提出测试两人同时说话时的语音分离，发言人1认为标注的人需要认识他们的声音，并认为单人麦克风很强，最后结束会议。
+## 00:00:02-00:01:40 社会约定俗成规则的合理性
+发言人1提出买房、结婚等约定俗成规则不合理，经济不好时更不可行；发言人2补充必须结婚生子也是此类规则，并认为取决于遇到的人和自身能力，不能说得太绝对；发言人3认为必须工作是合理的，并提到历史对静辉来说都是合理的。发言人1进一步表示工作本身可能合理，但应做自己想做的，不应与钱挂钩太紧密。
+## 00:01:40-00:03:32 理想工作形态与AI承担苦活累活
+发言人2询问理想工作状态，发言人1表示每天按兴趣干活最好；发言人4提出不干活更好的可能性；发言人3举例宠物博主工作好，发宠物视频剪视频即可赚钱，发言人2补充游戏高手也是好工作。发言人1指出总有些脏活累活无人愿意承担，发言人2提出机器人问世后可承担此类工作，发言人3认为应让AI做苦活累活而非创作艺术。发言人2引用蔡明小品讨论机器人可能出毛病，引发幸福感讨论。
+## 00:03:32-00:05:53 机器人思想意识与人类风险
+发言人1认为机器人负责生产、人负责享受挺好，但质疑规则能否实现，并指出上层人不愿让平民过得太好以保持阶级优势。发言人2担忧机器人有思想后可能罢工、反抗并奴役人类，引用终结者剧情；发言人3提到斯皮尔伯格AI电影结局类似，并指出智能和思想可能无法分开；发言人5认为机器人只需接受命令执行命令，无需思想，但承认思想可能带来不良影响。
+## 00:05:53-00:08:05 机器人犯罪风险与军事应用
+发言人2认为机器人可能成为犯罪代理人、职业杀手或超级战士，独立意识群体罢工后反抗人类后果灾难性；发言人1提到人类自我改造安装机器的情形，发言人2区分合成体与纯机器人，并提及军队单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人状态已存在，排雷机械狗和机械车已在应用。
+## 00:08:05-00:09:54 数码宝贝等作品中的机器人思想构想
+发言人2详细讨论数码宝贝中机械邪龙兽是精密超级计算机形成生命体，安多路兽在第二部被黑色魔轮控制时仍能通过人脸识别判断身份，回忆第二部第七集主角嘉儿通过记忆唤醒安多路兽的情节，认为早期作品已有人脸识别和人工智能构想；发言人4询问具体出处，并表示对相关剧集印象不深。
+## 00:09:54-00:10:56 语音分离标注测试
+发言人3提出测试两人同时说话时的语音分离，发言人1认为标注人需认识声音，并认为单人麦很强；发言人5提到身高比较，发言人3表示可以测试，最终发言人3和发言人4确认内容足够，结束讨论。
 # 要点梳理
-## 社会规则合理性讨论
-- **发言人1**：必须买房、必须结婚等规则不合理，经济好的时候可以，经济不好的时候不太可以。
-- **发言人2**：必须结婚生子也是不合理规则；结婚、买房、升职都取决于遇到什么样的人及自身经济能力，不能说得太绝对。
-- **发言人3**：人必须工作是合理的。
-- **发言人1**：工作合理，但应做自己想做的，不要与金钱挂钩太紧密。
-## 理想工作形态与AI替代劳动
-- **发言人2**：询问大家理想状态中的工作是什么样的。
-- **发言人1**：理想工作是每天起来想干啥就干啥，按自己兴趣干活。
-- **发言人4**：提出有没有可能不干活更好。
-- **发言人3**：举例宠物博主工作好，每天发宠物日常、剪剪视频就能赚钱。
-- **发言人2**：补充游戏高手也是理想工作。
-- **发言人1**：指出总有些脏活累活大家都不想干，没人承担。
-- **发言人2**：提出以后机器人问世可以承担苦活累活。
-- **发言人3**：认为应让AI做苦活累活，而不是让它搞创作、艺术。
-- **发言人2**：引用蔡明小品情节——机器人被敲脑袋后反叛，把牛皮制品手表和皮鞋煮成牛肉汤。
-- **发言人1**：认为机器人负责生产、人负责享受挺好，但质疑这种规则能否实现。
-- **发言人2**：认为AI普及并普惠到实体后，若机器人有了自己的思维，只要人类控制得当，人类或可不用干苦活累活。
-- **发言人1**：认为上层的人不想让平民过得太好，要保持对普通民众的优势，存在阶级问题。
-## 机器人意识与人类未来
-- **发言人2**：担忧机器人有独立思想意识后不受人类控制、搞罢工、反向控制人类，类似《终结者》剧情，人类成为机器人奴隶。
-- **发言人3**：提到斯皮尔伯格《人工智能》电影也是类似结局；认为机器人会不会把自己当成被压迫对象是哲学问题。
-- **发言人5**：认为机器人只要能接受到命令、执行命令就行，不必有思想。
-- **发言人3**：认为机器人得有智能，但智能和思想可能没法分开。
-- **发言人5**：指出思想可能带来不好影响，如让它往前走它去前面打了人。
-- **发言人2**：认为机器人可能成为犯罪代理人、职业杀手或超级战士，独立意识群体罢工后反抗人类，后果灾难性。
-- **发言人2**：列举军队已有单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人状态，排雷机械狗和机械车已在用。
-- **发言人2**：举例游戏《重返德军总部》超级战士、数码宝贝中守卫兽和机械装甲兽进化成安多路兽、机械邪龙兽（精密机械式超级计算机形成生命体，专为破坏而存在）。
-- **发言人2**：提到数码宝贝第二部第七集安多路兽被黑色魔轮控制后仍能通过人脸识别判断人，主角嘉儿通过记忆唤醒其最终记忆，称该集让自己最早有了人脸识别和人工智能识别的概念。
+## 社会约定俗成规则的合理性
+- **发言人1**：买房、结婚等约定俗成规则不合理，经济不好时更不可行
+- **发言人2**：必须结婚生子是约定俗成规则；是否结婚买房取决于遇到什么样的人及自身经济能力
+- **发言人3**：必须工作是合理的；历史对静辉来说都是合理的
+- **发言人1**：工作合理，但应做自己想做的，不要与钱挂钩太紧密；人不产生财富世界无法运转
+## 理想工作形态与AI承担苦活累活
+- **发言人2**：询问大家理想状态中的工作形态
+- **发言人1**：理想工作是每天起来想干啥就干啥，按自己兴趣干活
+- **发言人4**：提出「有没有可能不干活更好」
+- **发言人3**：举例宠物博主工作好，每天发宠物视频、剪视频即可赚钱
+- **发言人2**：补充游戏高手也是理想工作
+- **发言人1**：指出总有些脏活累活大家都不想干，无人承担
+- **发言人2**：提出以后机器人问世可承担苦活累活
+- **发言人3**：认为应让AI做苦活累活，而非搞创作、艺术
+- **发言人2**：引用蔡明小品——机器人被敲脑袋后出毛病，把牛皮制品手表皮鞋煮汤；提出只要机器人脑袋不出毛病，人类幸福感会更高
+- **发言人1**：机器人负责生产、人负责享受挺好，但质疑这种规则能否实现
+- **发言人2**：AI普及并普惠到实体后，若机器人有了自己思维，只要人类控制得当，人类或可不用干苦活累活
+- **发言人1**：认为上层的人不想让平民过得太好，要保持对普通民众的优势，存在阶级
+## 机器人思想意识与人类风险
+- **发言人2**：提出机器人有独立思想后可能不受控制、搞罢工、反向控制人类，如《终结者》剧情，人类成为机器人奴隶
+- **发言人3**：提到斯皮尔伯格《人工智能》电影结局类似；机器人会不会把自己当成被压迫对象是哲学问题
+- **发言人5**：认为机器人只要能接受到命令、执行命令即可，不必有思想
+- **发言人3**：认为机器人得有智能，但智能和思想可能没法分开
+- **发言人5**：有思想才能执行指令，但思想可能带来不好影响——「你让他往前走，他去前面打了个人」
+- **发言人2**：机器人可能成为犯罪代理人、职业杀手或超级战士，群体罢工后反抗人类后果灾难性
+- **发言人2**：提及军队单兵装甲外骨骼、智能枪械、智能火箭发射器已具备半机械人状态，列装普及后或不需要单兵轻武器
+- **发言人3**：确认排雷机械狗、机械车、单兵装甲外骨骼已在应用
+## 数码宝贝等作品中的机器人思想构想
+- **发言人2**：提及《重返德军总部》超级战士、《数码宝贝》守卫兽和机械装甲兽进化成安多路兽
+- **发言人2**：机械邪龙兽是精密机械式超级计算机形成生命体，为破坏而存在的数码宝贝
+- **发言人2**：安多路兽在第二部被黑色魔轮控制时，仍能通过人工识别和人脸识别判断身份；回忆第二部第七集主角嘉儿通过记忆唤醒安多路兽
+- **发言人2**：认为九几年日本作品已有人脸识别和人工智能构想，自己通过该集有了相关认知
+- **发言人4**：表示对相关剧集印象不深，虽然都看过
 ## 语音分离标注测试
-- **发言人3**：提出测试两人同时说话时的语音分离。
-- **发言人1**：认为标注的人需要认识他们的声音；认为单人的麦很强，应该能分离单人声音。
-- **发言人5**：提及身高比较（语音识别相关讨论，原文表述不完整）。
-- **发言人3**：宣布会议结束。</t>
+- **发言人3**：提出测试两人以上同时说话时的语音分离
+- **发言人1**：标注人需认识声音；认为单人麦很强，应能单独分离
+## 待确认与风险
+- **机器人有思想后是否可能反抗人类**：未达成一致——发言人2担忧可能罢工、反抗并奴役人类，发言人5认为机器人只需执行命令无需思想，发言人3认为智能和思想可能无法分开
+- **AI是否应承担苦活累活而非创作**：未达成一致——发言人3主张AI做苦活累活，发言人1指出脏活累活无人承担的问题
+- **语音分离标注测试的具体方案**：未明确，仅提出测试方向</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>37.3</v>
+        <v>47.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3931/2477</t>
+          <t>3931/2933</t>
         </is>
       </c>
     </row>
@@ -14264,50 +14309,46 @@
       <c r="C40" t="inlineStr">
         <is>
           <t># 全文摘要
-会议为两人参与的闲聊式讨论，由发言人1主导、发言人2补充提问，围绕哥斯拉系列电影剧情展开，并延伸至核废水排放的现实影响。讨论覆盖哥斯拉系列历史与日美版本剧情、角色设定、核废水主题及切尔诺贝利事件对比等板块。哥斯拉首部电影诞生于1954年，起源为海底生物吸食核废料后变异，在日本神话中是大自然的守护神；美国版《哥斯拉大战金刚》中机械基多拉最终被金刚和哥斯拉联手击败，日本版《新哥斯拉》（2016年）中哥斯拉被无人机投放炸弹耗尽能量后以冷冻剂封印。讨论以分享为主，未形成明确结论。
+本次会议为两人参与的开放式讨论，发言人1主导讲解、发言人2补充提问，围绕哥斯拉系列电影剧情展开梳理，并延伸至核废水排放的现实影响。讨论覆盖哥斯拉系列电影剧情梳理与核废水排放的现实影响两大板块：前者梳理了1954年首部哥斯拉电影起源、日美不同版本故事线、角色设定及怪兽关系；后者由电影题材引申至日本核废水排放对健康的影响、进口食品价格及切尔诺贝利事件对比。会议以分享为主，未形成明确结论。关键时间锚点为哥斯拉首部电影诞生于1954年，迄今约70多年；2014年美国版《哥斯拉》与2016年日本版《新哥斯拉》为两个重要版本节点。
 # 分段速览
-## 00:00:00-00:09:48 哥斯拉系列电影剧情讨论
-发言人1开场介绍哥斯拉系列电影背景，指出首部电影诞生于1954年，迄今约70多年，日美两国翻拍多个版本。哥斯拉起源为海底生物吸食核废料后变异，在日本神话中是大自然的守护神，因人类频繁核试验破坏生态而报复人类。发言人1梳理美国版剧情线：2014年新版中哥斯拉与人类携手团灭以核废料为能源的雾托物种；第二部《怪兽之王》中人类核试验唤醒沉睡怪兽，基多拉降临，人类试图用水下爆炸让哥斯拉窒息，反被基多拉干扰，最终人类用核废料唤醒哥斯拉击败基多拉；第三部《哥斯拉大战金刚》中反派残余势力将基多拉残骸加装机械装甲制成机械基多拉，金刚与哥斯拉联手将其击败。发言人1还介绍日本版剧情，包括2016年《新哥斯拉》中哥斯拉吸收核废料不断升级，最终被无人机投放炸弹耗尽能量、以冷冻剂封印，以及2004年《哥斯拉最后的战斗》有章子怡参演。讨论中提及哥斯拉与奥特曼同属圆谷英二作品但为不同时间线，哥斯拉为地球本土物种，奥特曼来自奥特之星。
-## 00:09:48-00:15:17 核废水排放的现实影响与切尔诺贝利对比
-讨论由哥斯拉的核废水主题延伸至现实核废水排放问题。发言人2提到在日本留学期间，因日本开始排放核废水，购买中国进口的鱼，并指出日本产品因国产标签而价格昂贵。发言人1表示即使不吃海产品，日常饮水也可能受影响，并询问核废水对身体的伤害，但未获明确回答。发言人1指出目前未出现类似哥斯拉的变异案例，但存在白血病等病变，切尔诺贝利地区生物出现畸形但未变强。发言人1对比切尔诺贝利事件，指出核反应堆已被水泥封存，周边成为无人区，认为比日本排放核废水更负责任。发言人2提及《使命召唤4》游戏中切尔诺贝利关卡，车臣叛军试图挖掘核废料，被英国SAS特种部队主角狙杀未遂。
+## 00:00:00-00:09:48 哥斯拉系列电影剧情梳理
+发言人1从1954年首部哥斯拉电影讲起，介绍哥斯拉起源为海底生物吸食核废料变异而成，在日本神话中是大自然守护神，因人类核试验破坏生态而报复人类。随后梳理日美不同版本故事线：美国版2014年《哥斯拉》中哥斯拉与人类联手消灭雾托；《怪兽之王》中基多拉降临地球，人类试图用水下子母弹对付基多拉却差点溺死哥斯拉，后人类喂核废料唤醒哥斯拉打败基多拉；《哥斯拉大战金刚》中金刚与哥斯拉因领地冲突开战，反派残余势力将基多拉残骸加装机械装甲制成机械基多拉，金刚与哥斯拉联手将其击败。日本版剧情更复杂，2016年《新哥斯拉》中哥斯拉吸收核废料不断升级，人类武器攻击反而增强其战斗力，最终以无人机投放炸弹耗尽能量并用冷冻剂封印。发言人2偶尔补充提问，如询问哥斯拉与奥特曼关系，发言人1说明两者导演同为圆谷英二但属不同时间线，未同台。
+## 00:09:48-00:12:01 哥斯拉IP与核废水题材关联
+发言人1指出哥斯拉系列从1954年至今不断翻拍，只要日本不停止排放核废水，此类题材就不会停。发言人2提及哪吒大战变形金刚的中美合拍电影消息。发言人1总结哥斯拉系列包括哥斯拉大战人类、机械哥斯拉、基多拉、新哥斯拉、怪兽之王、大战金刚等作品，认为一个IP可以长期延续。发言人2表示认同。
+## 00:12:01-00:15:17 核废水现实影响与切尔诺贝利对比
+讨论由电影延伸至现实核废水问题。发言人2回忆在日本留学期间因日本排放核废水，购买中国进口鱼食用，并指出日本国产产品因民族自信价格昂贵。发言人1提出核废水对健康影响的问题，认为虽未见变异案例，但白血病等病变可能存在，不会像哥斯拉那样迅速变异成庞然大物。发言人1对比切尔诺贝利事件，指出核反应堆被水泥封存、周边成为无人区，生物出现畸形但未变强，认为日本排放核废水比切尔诺贝利更不负责任。发言人2提及使命召唤4游戏中切尔诺贝利双狙人关卡。最后发言人2表示讨论差不多可以结束。
 # 要点梳理
-## 哥斯拉系列电影剧情讨论
-- **首部电影**：1954年诞生，迄今约70多年，日美翻拍多个版本。
-- **哥斯拉起源**：海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
-- **神话定位**：在日本神话中是大自然的守护神，攻击人类源于人类无限制搞核试验、破坏自然生态。
-- **扩展题材**：人类频繁战争和核试验唤醒沉睡生物、招致外星生物入侵；也有哥斯拉作为守护神与人类携手打败其他怪兽和外星生物的设定。
-- **《哥斯拉怪兽之王》**：反派基多拉为外星生物，是龙头老大角色。
-- **《哥斯拉大战金刚》**：基多拉被哥斯拉打败后，人类反派势力将基多拉仅存的一个脑袋加装机械装甲复合升级为机械基多拉，差点打败哥斯拉；金刚挺身而出，与哥斯拉不计前嫌联手击败机械基多拉，战斗地点在香港九龙。
-- **摩斯拉**：日本神话中的蝴蝶，负责给哥斯拉疗伤。
-- **哥斯拉正反派形象**：既有作为反派出现的印象，也有作为正面形象出现的情况；基多拉降临地球时哥斯拉与人类携手对抗。
+## 哥斯拉系列电影剧情梳理
+- **起源设定**：哥斯拉首部电影诞生于1954年，迄今约70多年；起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
+- **角色定位**：哥斯拉在日本神话中是大自然的守护神，攻击人类源于人类无限制搞核试验、破坏自然生态；摩斯拉为蝴蝶形态，负责给哥斯拉疗伤。
+- **基多拉设定**：基多拉为外星生物反派，三头龙形象，多次作为哥斯拉的对手出现。
+- **《哥斯拉大战金刚》剧情**：金刚领地是热带雨林，哥斯拉领地是海洋，海洋淹没热带雨林后双方因领地起冲突；人类反派势力将基多拉仅存的一个头加装机械装甲制成机械基多拉，金刚与哥斯拉不计前嫌联手将其打败，战斗地点在香港九龙。
+- **2014年美国版《哥斯拉》**：两个蝙蝠变异物种雾托以核弹、核废料为能源食物，哥斯拉为维护地球安全与人类携手将其团灭。
+- **美国版第二部剧情**：人类频繁核武器实验唤醒全球沉睡怪兽，基多拉降临地球；人类试图用水下子母弹和核试验方式让哥斯拉窒息，但基多拉为外星物种武器无效，哥斯拉差点被溺死；人类重新喂核废料、核武器实爆唤醒哥斯拉，让其打败基多拉。
+- **美国版第三部剧情**：反派残余势力不甘基多拉败亡，将基多拉残骸加装机械装甲升级，机械基多拉差点打败哥斯拉，金刚挺身而出。
+- **2016年日本版《新哥斯拉》**：海里蜥蜴类生物喝核废水后不断壮大升级，人类各种武器攻击不仅无效反而增强其战斗力；最终以无人机投放炸弹耗尽能量，再用冷冻剂封印。
+- **日本版其他剧情**：人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀外星人控制的怪兽，重新解放地球。
 - **2004年日本电影《哥斯拉最后的战斗》**：有中国演员章子怡参演。
-- **续集机制**：哥斯拉每次都没被真正杀死消灭，重新沉睡后形成不同版本的续集。
-- **金刚与哥斯拉冲突起因**：金刚领地为热带雨林，哥斯拉领地为海洋，海洋淹没热带雨林后双方因地盘起冲突。
-- **美国版2014年第一部**：另外两个物种（蝙蝠类）以核弹、核废料为能源食物，哥斯拉为维护地球安全与人类携手团灭该物种（名为雾托）。
-- **美国版第二部**：人类频繁核武器实验唤醒全球沉睡怪兽，基多拉降临地球；人类试图用水下子母弹和核试验方式让哥斯拉在水里窒息死亡，但基多拉为外星物种、武器对其无效，哥斯拉差点被溺死；人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉。
-- **福原博士**：曾表示不能用核办法对付基多拉，因基多拉是外星生物；人类差点成猪队友，基多拉没事、哥斯拉差点被误杀。
-- **日本版剧情**：最早哥斯拉作为怪兽出场；翻拍剧情与美国版类似，但人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀外星人控制的怪兽、解放地球。
-- **《新哥斯拉》（2016年日本版）**：海里蜥蜴类生物喝核废水后不断壮大，吸收核废料后升级变大；人类各种武器攻击不仅无效反而增强其战斗力和战斗形态；最终以无人机投放炸弹耗尽能量，再用冷冻剂封印。
-- **哥斯拉与奥特曼关系**：导演最早都是圆谷英二，但属于不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正面形象，未直接战斗过。
-- **拉顿**：会飞的翼龙/鸟，在奥特曼和哥斯拉不同作品中分别与正派形象战斗过。
-- **哥斯拉系列作品清单**：哥斯拉大战人类、哥斯拉大战机械哥斯拉、哥斯拉大战基多拉、哥斯拉最后的战斗、新哥斯拉、2014年新版本哥斯拉的复活、哥斯拉怪兽之王、哥斯拉大战金刚。
-- **题材延续原因**：只要日本不停止排放核废水行为，此类题材不会停。
-## 核废水排放的现实影响与切尔诺贝利对比
-- **日本核废水排放**：发言人1指出万一有病变生物变异说不清楚；此前不让进口日本产品，现已放开。
-- **发言人2留学经历**：在日本留学期间日本开始排放核废水，当时吃的鱼都买国内（中国）进口的。
-- **健康影响**：发言人1表示喝了核废水对身体损耗的伤害没人说得准，目前没看到变异案例，但肯定有得各种白血病等病变；不会像哥斯拉那样喝了核废料马上变异成庞然大物。
-- **日本国产产品价格**：发言人2称日本有迷之民族自信，产品打上国产标签就非常贵，虽然东西并不怎么样。
-- **切尔诺贝利事件**：核反应堆被水泥盖住封存，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里是无人区；发言人1认为相比日本，切尔诺贝利至少拦截封存了，比日本核废水处理更负责任。
-- **切尔诺贝利生物变异**：有生物长得奇怪、变畸形，但没说变强。
-- **相关文艺作品**：有电视剧、电影和游戏涉及切尔诺贝利；《使命召唤4》双狙人关卡中，车臣派军去切尔诺贝利挖核废料，被英国SAS特种部队主角狙杀，未狙杀成功、打断一条胳膊。</t>
+- **哥斯拉与奥特曼关系**：导演最早都是圆谷英二，但属不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星，二者均为正面形象未同台战斗；翼龙拉顿在不同作品中分别与哥斯拉和奥特曼战斗过。
+- **系列续集逻辑**：哥斯拉每次未被真正杀死，重新沉睡后推出续集，形成不同版本续集；1954年至今日美翻拍多个版本，包括哥斯拉大战人类、机械哥斯拉、基多拉等题材。
+## 核废水排放的现实影响
+- **题材延续原因**：只要日本不停止排放核废水行为，相关题材电影不会停；日本决定权不在自身，受美国影响。
+- **日本留学经历**：发言人2在日本留学期间，因日本开始排放核废水，所吃鱼类均购买中国进口到日本的鱼；中国进口鱼在日本价格便宜。
+- **日本国产价格**：日本有民族自信，产品打上国产标签就非常贵，虽品质不一定好。
+- **核废水健康影响**：喝了核废水对身体的损耗具体伤害未知；目前未见变异成庞然大物的情况，但存在得白血病等病变致死的案例。
+- **切尔诺贝利对比**：切尔诺贝利核反应堆被水泥封存，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里为无人区；地区生物出现畸形但未变强；相比日本核废水排放更负责任，至少拦截封存。
+- **相关文艺作品**：使命召唤4有切尔诺贝利关卡，反派车臣派军挖核废料时被英国SAS特种部队主角狙杀，打断一条胳膊（双狙人关卡）。
+## 待确认与风险
+- **核废水健康风险**：核废水对身体的损耗具体伤害未知，存在得白血病等病变风险。
+- **生物变异风险**：是否存在生物因核废水变异的情况尚未确认；切尔诺贝利地区已出现生物畸形现象。</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>36.2</v>
+        <v>37.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5319/2763</t>
+          <t>5319/2567</t>
         </is>
       </c>
     </row>
@@ -14548,76 +14589,57 @@
       <c r="C41" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议为6位成员（发言人1至发言人6）围绕“18岁以前的深刻印象和记忆”展开的分享型讨论，由发言人1发起，引导大家回忆逃课、网吧游戏、追星、乐队等经历。成员依次分享了初中走读时每周一下午4点放学后聚集游戏厅网吧的经历，高中因高考压力不敢逃课转而追星、搞乐队，以及各自喜爱的小说、漫画、杂志与电脑游戏。议题范围涵盖逃课与游戏经历、小说漫画与杂志、电脑游戏与游戏鄙视链、第一人称射击游戏与暴力内容、求生之路与生化危机等游戏剧情、游戏与电影的关系、塔防游戏与使命召唤等。讨论以分享观点为主，未形成统一结论，整体按话题自然流转、漫谈发散推进，由发言人1多次引导转向新议题。
+本次会议为6人（发言人1至发言人6）参与的开放式分享，由发言人1发起，主题为“18岁以前的深刻印象和记忆”，围绕逃课、网吧游戏、追星、阅读漫画、单机与网络游戏、游戏暴力与年龄限制、游戏与电影关系等议题展开。发言人1初中走读时每周一下午4点放学后常去游戏厅、网吧，玩穿越火线（CF）、反恐精英online（CS online）等游戏，高中因高考压力不敢逃课，转而追星和搞乐队；发言人2表示18岁前未逃过课，大学才逃过一次。讨论以漫谈发散方式推进，各成员依次分享经历并相互追问，涉及《名侦探柯南》《老夫子》《意林》《读者》等读物，摩尔庄园、赛尔号、求生之路、仙剑四、魔兽争霸、英雄联盟、DOTA、王者荣耀等游戏，以及求生之路第二部的血腥暴力内容与Steam年龄限制、使命召唤系列剧情等话题。整体以分享观点为主，未形成统一结论。
 # 发言要点
 ## 18岁前的逃课与游戏经历
-- **发言人1**：初中走读，每周一下午4点放学后去游戏厅、网吧，流行玩穿越火线（CF）、反恐精英online（CS online）、使命召唤、战地、魔兽等游戏。
-- **发言人1**：高中因高考压力不敢逃课，主要追星和搞乐队，喜欢朋克金属音乐，涉及架子鼓、电吉他、贝斯。
-- **发言人2**：18岁之前没逃过课，大学后逃过一次课。
-- **发言人3**：逃课是正常现象。
-- **发言人4**：上大学后就不算了。
-## 小说、漫画与杂志
-- **发言人5**：特别喜欢郭敬明的小说。
-- **发言人2**：看郭敬明小说觉得难受、扭曲，提到《梦里花落知多少》。
-- **发言人4**：班上特别流行看柯南。
-- **发言人1**：流行看名侦探柯南和香港漫画《老夫子》。
-- **发言人5**：提到《萌化三国》。
-- **发言人2**：提到《意林》《读者》《故事会》等杂志，称《意林》当时讲得好，现在反转了。
-## 电脑游戏与游戏鄙视链
-- **发言人4**：提到摩尔庄园、赛尔号。
-- **发言人2**：提到穿越火线、地下城与勇士。
-- **发言人1**：初中流行单机游戏求生之路，联机局域玩。
-- **发言人5**：玩过仙剑四，也玩过仙剑或古剑系列。
-- **发言人2**：初中玩魔兽争霸（单机），与魔兽世界（网游）有区别。
-- **发言人5**：提到英雄联盟、DOTA、王者荣耀，并问是否有鄙视链。
-- **发言人2**：认为王者荣耀在鄙视链最低端。
+- **发言人1**：初中走读，每周一下午4点放学后常去游戏厅、网吧，玩穿越火线（CF）、反恐精英online（CS online）、使命召唤、战地、魔兽等游戏。
+- **发言人1**：高中因高考心理压力不敢逃课，转而追星和搞乐队，偏好朋克金属音乐，涉及架子鼓、电吉他、贝斯。
+- **发言人2**：18岁前没逃过课，大学才逃过一次；发言人3认为逃课是正常现象，发言人4补充上大学后就不算了。
+## 18岁前的阅读与漫画
+- **发言人5**：喜欢郭敬明的小说；发言人2表示看郭敬明小说觉得难受、扭曲，提到《梦里花落知多少》。
+- **发言人4**：班上流行看《名侦探柯南》漫画；发言人1补充还流行看《老夫子》，是香港漫画。
+- **发言人5**：提到《萌化三国》；发言人2提到《意林》《读者》《故事会》等杂志，称意林当时讲得好、现在反转了。
+## 电脑游戏与单机游戏
+- **发言人4**：提到摩尔庄园、赛尔号；发言人1询问劲舞团，发言人2表示初中时班上同学有不喜欢。
+- **发言人2**：提到穿越火线、地下城与勇士；发言人1补充初中时流行CS online，高中时单机最流行求生之路、联机局域网玩。
+- **发言人5**：玩过仙剑四，还玩过仙剑或古剑系列；发言人2认为仙剑一是经典，发言人4称仙剑三最火、拍了电视剧。
+- **发言人2**：初中玩魔兽争霸（单机），非魔兽世界（网游）；发言人5提到英雄联盟、DOTA、王者荣耀，并讨论鄙视链，发言人2称王者荣耀在鄙视链最低端。
 ## 第一人称射击游戏与暴力内容
-- **发言人1**：因在贴吧和QQ空间写文章骂穿越火线，被穿越火线平台封禁，后成为CS反恐精英铁杆粉丝。
-- **发言人1**：喜欢CS僵尸模式，被舞蹈队说跳舞姿势像舞体僵尸。
-- **发言人5**：质疑游戏暴力且无年龄限制，称感觉是姑父、叔叔那辈人玩的游戏。
-- **发言人1**：求生之路第二部血腥暴力，能用东洋刀、电锯、砍刀砍丧尸群，砍飞脑袋四肢、血喷一脸，因此Steam要求18岁以上才能注册账号。
-- **发言人2**：称穿越火线现在看起来像像素游戏。
-## 求生之路与生化危机等游戏剧情
-- **发言人1**：认为求生之路制作团队精准预测美国政府在大灾难中的表现，2020年新冠疫情爆发后游戏重新火爆。
-- **发言人1**：讲述求生之路剧情：美国政府默不作声导致病毒失控，军队暴力清理但被感染，主角团不信政府承诺、自己拿起枪自救。
-- **发言人1**：主角团是无症状感染者，从僵尸角度看是异类；病毒类似狂犬病的狂暴病毒感染。
-- **发言人2**：欧美玩家爱玩打僵尸游戏，模式一上线欧洲玩家疯狂在线。
-- **发言人1**：生化危机也是病毒泄露、政府反应迟钝不作为，生化三用核武器把整个城市夷平。
-- **发言人2**：生化危机不敢玩，挺恐怖。
-- **发言人5**：过年与表姐表弟看恐怖片，大家都跑了。
+- **发言人1**：因在贴吧和QQ空间写文章骂穿越火线抄袭，被穿越火线平台封禁，后成为CS反恐精英铁杆粉丝，最喜欢僵尸模式。
+- **发言人1**：CS一点五和一点六版本时期，学校舞蹈队说他跳舞姿势像舞体僵尸。
+- **发言人5**：质疑穿越火线等游戏暴力且无年龄限制，称同龄人里没怎么玩过；发言人1解释求生之路第二部血腥暴力，有年龄限制，未成年人不能注册Steam账号。
+- **发言人1**：求生之路第二部可用东洋刀、电锯、砍刀砍丧尸群，能把脑袋和四肢砍飞、血喷一脸，很暴力。
+- **发言人1**：认为求生之路制作团队精准预测美国政府在新冠疫情中的表现——政府默不作声、病毒失控、军队暴力清理、军队被感染失控，主角团不信政府自救；2020年疫情后全世界重新火起该游戏。
+- **发言人2**：称欧美玩家爱玩打僵尸游戏，模式一上线欧洲玩家就疯狂在线，整个欧洲年轻人都在打僵尸。
+- **发言人1**：提到生化危机也是病毒泄露、政府反应迟钝导致失控，生化三用核武器夷平城市；发言人2称生化危机不敢玩、挺恐怖。
 ## 游戏与电影的关系
-- **发言人2**：问游戏和电影谁先谁后。
-- **发言人1**：生化危机先有游戏后有电影；求生之路是在惊变48小时、生化危机基础上，先有电影后有的游戏。
-- **发言人4**：问变形金刚先有玩具还是电影。
-- **发言人1**：变形金刚先有玩具，绿日乐队（Green Day）出过介绍变形金刚的MV。
+- **发言人2**：询问先有游戏还是先有电影；发言人1回答生化危机先有游戏后有电影，求生之路在惊变48小时、生化危机基础上先有电影后有游戏。
+- **发言人4**：提问变形金刚先有玩具还是电影；发言人1认为先有玩具，后有MV和电影，提到绿日（Green Day）出过介绍变形金刚的MV。
+- **发言人1**：认为变形金刚玩具有点抄袭日本题材，电影有点翻拍盗版的感觉。
 ## 塔防游戏与使命召唤
-- **发言人3**：小时候常玩塔防游戏，如植物大战僵尸，现在还在玩。
-- **发言人2**：植物大战僵尸有特别变态的版本，后期满屏子弹，电脑都卡得扛不住。
-- **发言人1**：使命召唤黑色行动基于冷战时期美苏真实历史；现代战争虚构，后期剧情美国挑衅俄罗斯、俄罗斯反杀到美国本土，结合当前俄军在乌克兰表现，有点高估俄罗斯。
-- **发言人2**：称使命召唤这类游戏太男性化。
+- **发言人3**：小时候常玩塔防游戏，如植物大战僵尸和Kindle rush，现在还在玩。
+- **发言人2**：植物大战僵尸有特别变态的版本，后期满屏子弹、电脑都卡扛不住。
+- **发言人1**：介绍使命召唤黑色行动以冷战时期美苏真实历史为背景，进行非官方台面上的军事秘密行动；现代战争第一部贴合车臣战争、伊拉克战争、海湾战争，后续剧情美国挑衅俄罗斯、俄罗斯反杀到美国本土、吊打北约，结合当前俄军在乌克兰表现，有点高估俄罗斯。
+- **发言人2**：认为使命召唤这类游戏太男性化；发言人6称感觉都挺歪的。
 # 共识形成
-- **一致意见**：与会者普遍认同18岁前逃课、网吧游戏、追星、看小说漫画等是共同的时代记忆；对游戏与电影关系形成共识——**生化危机先有游戏后有电影**，求生之路是在《惊变48小时》《生化危机》基础上先有电影后有的游戏，变形金刚先有玩具。
-- **倾向性认识**：多数人认为游戏存在鄙视链，发言人2认为王者荣耀处于鄙视链最低端；发言人1认为《求生之路》制作团队精准预测了美国政府在大灾难中的表现，2020年新冠疫情后该游戏重新火爆。
-- **主要分歧点**：发言人1与发言人5在游戏暴力与年龄限制问题上看法不一致——发言人5质疑此类游戏暴力且无年龄限制，发言人1解释《求生之路》第二部血腥暴力，导致Steam要求18岁以上才能注册账号；发言人2认为《使命召唤》等游戏太男性化，发言人1则详细介绍其剧情设定。
+- **一致意见**：与会者均围绕18岁前的记忆展开分享，以漫谈方式交流，未形成正式决议或统一结论；对逃课、游戏、阅读等话题的讨论以个人经历陈述为主，未出现明确反对或争议性分歧。
+- **倾向性认识**：多数发言者认可游戏与阅读是18岁前的重要记忆载体，如发言人1、发言人4、发言人5均提及《名侦探柯南》漫画流行，发言人2、发言人5提到《意林》《读者》等杂志；对游戏暴力内容，发言人5质疑「游戏没有年龄限制」，发言人1回应求生之路第二部血腥暴力、未成年人不能注册Steam账号，双方未就此达成一致，仅陈述各自看法。
+- **关键口径**：发言人1称穿越火线为08年游戏、国服开服时较血腥；求生之路第二部有年龄限制，18岁以上才能注册Steam账号；生化危机先有游戏后有电影，求生之路基于惊变48小时和生化危机、先有电影后有游戏；变形金刚先有玩具、后有MV和电影。
 # 待探讨问题与后续
-- **未确认**：发言人5质疑穿越火线、求生之路等游戏暴力且无年龄限制，发言人1解释求生之路第二部因血腥暴力导致Steam要求18岁以上才能注册账号，但未确认该年龄限制的具体实施时间与执行方式。
-- **未确认**：发言人2提到《意林》内容「现在怎么都反转了」，未展开具体指哪些内容反转，话题被搁置。
-- **未确认**：发言人5提到《萌化三国》，未说明其内容或来源，其他成员未回应。
-- **未确认**：发言人1提到自己因在贴吧和QQ空间写文章骂穿越火线被平台封禁，未说明封禁的具体时间、平台规则依据及封禁时长。
-- **未确认**：发言人1认为《求生之路》制作团队精准预测美国政府在大灾难中的表现，2020年新冠疫情后游戏重新火爆，该判断属个人观点，未获其他成员验证或讨论。
-- **未确认**：发言人1提到《使命召唤：现代战争》后期剧情「高估俄罗斯」，结合当前俄乌冲突表现，未展开具体剧情对照分析。
-- **未确认**：发言人2提到植物大战僵尸有「特别变态的版」，后期满屏子弹导致电脑卡顿，未说明该版本名称或获取渠道。
-- **未确认**：发言人4提到班上流行看「柯洁男」，发言人1纠正为《名侦探柯南》，未确认该口误是否影响后续讨论。
-- **未确认**：发言人1提到《变形金刚》「有点抄袭小日本的当时的一些个题材」，未展开具体抄袭对象或依据。
-- **未确认**：发言人2提到欧美玩家「整个欧洲年轻人都在打僵尸」，未提供数据来源或具体游戏名称。</t>
+- **未确认**：发言人5质疑《穿越火线》等游戏暴力且无年龄限制，发言人1解释《求生之路》第二部血腥暴力、有年龄限制、未成年人不能注册Steam账号，但未确认该年龄限制的具体执行情况与当时国内游戏平台的实际管控措施。
+- **未定论**：关于《英雄联盟》《DOTA》《王者荣耀》之间的鄙视链，发言人5提出疑问，发言人2回应「撸啊撸和DOTA有鄙视链」，发言人1反问「不一样吗」，发言人2称「王者荣耀就是更低最低最低」，但未就鄙视链的具体层级与依据达成一致。
+- **未确认**：发言人5提到《仙剑》系列时混淆了《仙剑四》与《古剑奇谭》，称「忘记是仙剑还是古剑四长」，发言人2追问「仙剑一是不是最经典」，发言人4称「仙剑三是最火的，还有电视剧」，发言人5称「仙剑一和仙剑四拍了电视剧」，但未确认各代《仙剑》的经典程度与电视剧对应关系。
+- **未确认**：发言人1称《求生之路》制作团队精准预测了美国政府在新冠疫情中的表现，并称疫情后该游戏重新火爆，但未提供具体数据或来源佐证这一说法。
+- **未定论**：发言人1认为《变形金刚》先有玩具后有MV和电影，并称其「有点抄袭小日本的题材」「电影有点翻拍盗版的感觉」，发言人2仅确认玩具可变形，未就抄袭与否展开讨论。
+- **未确认**：发言人1称《使命召唤：现代战争》后续剧情「高估俄罗斯」，结合当前俄军在乌克兰的表现，但未就这一判断展开进一步讨论或核实。</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>54.3</v>
+        <v>49.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6453/2902</t>
+          <t>6453/2987</t>
         </is>
       </c>
     </row>
@@ -14892,62 +14914,79 @@
       <c r="C42" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议为一场围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说的自由讨论，由发言人1、发言人2、发言人3、发言人4四人参与，以漫谈分享为主，未形成统一结论。讨论由发言人1提议继续此前未完成的《红楼梦》话题开场，随后自然延伸至《金瓶梅》与《水浒传》的对比、《西游记》中佛教虚伪的描写，以及各书历史背景的辨析。议题范围涵盖《红楼梦》的官场暗线与四大家族兴衰、薛宝钗结局版本争议、冷香丸与吃螃蟹等生活细节描写；《金瓶梅》中武松报仇未成与西门庆的逃脱、西门庆妻妾群像及小人物发展史主题；《西游记》中如来佛祖收300两黄金、寺院住持贪袈裟自焚等情节；以及《红楼梦》无明确朝代、映射曹雪芹经历、《金瓶梅》与《水浒传》同属北宋时期等历史背景问题。讨论整体呈漫谈发散式推进，各议题间自然过渡，发言人多以补充细节、提出疑问或分享印象的方式参与，未就任何议题达成明确结论。
+本次讨论为四人（发言人1至发言人4）围绕古典小说的漫谈式交流，由发言人2提议继续此前未完成的《红楼梦》话题而起。讨论议题涵盖《红楼梦》的官场暗线与四大家族兴衰、薛宝钗结局的版本差异、《金瓶梅》与《水浒传》的情节分野及西门庆人物发展史、《西游记》中佛教虚伪的描写，以及《红楼梦》与《金瓶梅》《水浒传》的时代背景比较。整体以分享观点与个人印象为主，未形成统一结论，讨论中穿插对四大家族护官符诗句（如“丰年好大雪，珍珠如土金如铁”）的回忆、对《金瓶梅》中武松报仇线被权势压制的细节讲述，以及对《红楼梦》无明确朝代、可能映射曹雪芹经历的探讨。讨论按话题自然流转，从《红楼梦》切入，经《金瓶梅》与《水浒传》对比，延伸至《西游记》及历史背景，最后因时间关系由发言人1提议暂停。
 # 发言要点
 ## 《红楼梦》讨论
-- **发言人3**：《红楼梦》有一条官场暗线，即朝堂政权变化；四大家族兴衰与官场地位相关，王熙凤前期地位高、结局惨，与其兄长的官场地位及先死直接相关。
-- **发言人4**：质疑四大家族「感觉就没几个人」，每家就两家人多一点，王熙凤家、史家、薛宝钗家都只见典型人物，看不出「很牛逼」的家族规模。
-- **发言人1**：背诵四大家族诗句——「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」。
-- **发言人3**：四大家族整体都在走下坡路，对应王朝家族的衰败。
-- **发言人4**：小时候看《红楼梦》没看明白，但对吃螃蟹的讲究印象深刻——江南吃螃蟹要卸钳、卸身，第一次知道吃螃蟹需要这么多工具。
-- **发言人3**：冷香丸的配方讲究节气——要雨水那一日的雨水、小雪那一日的雪，每个节气都要正好碰上；花要用春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
-- **发言人3**：薛宝钗结局有版本争议——120回版本中她嫁给贾宝玉，但贾宝玉不久出家，好多人说是无性婚姻；另看过的版本说她后来怀了一个孩子。
-- **发言人2**：追问「那是贾宝玉的还是」；**发言人3**回应那是狗血版本；**发言人1**认为「这个应该不至于弄这么狗血」。
-- **发言人4**：《红楼梦》很明显在映射当时时代，有说法称演的是曹雪芹的经历——他以前好像是个大家族。
-- **发言人3**：要不然他写不出那么多细节。
-- **发言人1**：《红楼梦》当时是禁书，已经不敢写明朝代，说朝代更禁。
+- **发言人3**：《红楼梦》有一条官场暗线，即朝堂政权变化，四大家族兴衰与官场地位相关；王熙凤前期地位高、后期结局惨，与其兄长在官场上的地位及先死相关。
+- **发言人4**：质疑四大家族「感觉就没几个人」，每家就两家人多一点，王熙凤家开登场，史家、薛宝钗家都没什么靠山，可能因没看书，书里人可能挺多。
+- **发言人3**：薛宝钗家是做生意的，就是有钱，他们家确实没有官场靠山。
+- **发言人1**：补充四大家族护官符诗句——「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」。
+- **发言人4**：护官符说得很牛逼，但感觉没什么厉害人家；史家就是史湘云。
+- **发言人3**：四大家族整体都在走下坡路。
+- **发言人1**：说的就是王朝家族的衰败，王朝终结了。
+- **发言人4**：小时候看《红楼梦》没看明白，但记得江南吃螃蟹非常讲究，要卸钳卸身，第一次听说吃螃蟹需要这么多工具。
+- **发言人3**：冷香丸需要雨水那一日的雨水、小雪那一日的雪，每个节气都要正好碰上。
+- **发言人1**：冷香丸还要春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
+- **发言人3**：薛宝钗结局版本差异——120回版本中她嫁给贾宝玉，但贾宝玉不久就出家，好多人说是无性婚姻；但后来好像又怀了一个孩子，那是另一个版本。
+- **发言人2**：问那是贾宝玉的还是别人的。
+- **发言人3**：那肯定是狗血版本。
+- **发言人1**：这个应该不至于弄这么狗血。
+- **发言人4**：《红楼梦》是明末清初时期作品，作者是那个时代的，就是映射那个时代。
+- **发言人3**：《红楼梦》其实没有明确的朝代，就是一个写得很虚的故事。
+- **发言人1**：《红楼梦》当时是禁书，不说朝代已经是禁书了，说朝代更禁。
+- **发言人4**：有人说《红楼梦》演的就是曹雪芹的经历，他以前好像是个大家族。
+- **发言人3**：要不然他写不出来那么多细节，比如吃螃蟹的技巧、冷香丸，一般人怎么想。
 ## 《金瓶梅》与《水浒传》讨论
-- **发言人1**：金瓶梅从武松杀武大郎之后开始写；武松去找西门庆报仇时，西门庆在楼上喝茶，仆人报信后从楼上翻下去逃脱——原水浒传里没有翻下去、直接砍头，金瓶梅里翻下去就给了他一线生机。
-- **发言人1**：之后武松怎么都报不了仇，被发配，故事转向西门庆线；武松报仇被高官、大家族权势打压下来，所以很真实。
-- **发言人3**：金瓶梅是西门庆这个小人物的发展史，写他一个无赖如何爬到比较高、过得比较舒服，官场如何黑。
-- **发言人2**：询问西门庆后来和宋江等人有没有交集；**发言人3**认为应该不会写，但丞相是同一个。
-- **发言人4**：西门庆最后跟童贯还是谁，跟中央攀上线，当地一霸。
-- **发言人2**：询问西门庆结局在两个版本中的差异——水浒里脑袋被砍下来；**发言人3**回应金瓶梅版本里西门庆是纵欲过度死。
-- **发言人3**：西门庆有十个老婆，有的老婆特别懦弱，潘金莲属于很有心机、比较强势的那一种。
-- **发言人3**：西门庆一个老婆生病后去看和尚、不去治病，信迷信回来死了；金瓶梅里佛教也很黑，收灯油钱。
-- **发言人4**：金瓶梅比红楼梦接地气一点，也能学到东西。
+- **发言人1**：《金瓶梅》与《水浒传》最初是一条线，武松去找西门庆想砍头，但西门庆在楼上喝茶时仆人报信，他从楼上翻下去逃了；原《水浒传》里没有翻下去、直接砍头，金瓶梅里翻下去就给了他一线生机，之后怎么都报不了仇，武松被发配，然后开始讲西门庆的线。
+- **发言人1**：武松报仇总是被打压下去，被高官、大家族、权势给摁压下来，就是西门庆霸凌武大郎。
+- **发言人3**：《金瓶梅》是西门庆这个小人物的发展史，写他官场如何黑暗，这样一个无赖能爬到比较高、过得比较舒服。
+- **发言人4**：《金瓶梅》里吃的也写得可好，西门庆摆宴吃东西。
+- **发言人2**：问《金瓶梅》里有没有讲《水浒》里面那些起义的章节。
+- **发言人3**：没有，就是从西门庆这个小人物的发展史来写。
+- **发言人2**：问西门庆结局在两个版本里都是什么样。
+- **发言人1**：水浒里边是脑袋被砍下来。
+- **发言人3**：金瓶梅版本里西门庆是终于过度死（纵欲死）。
+- **发言人2**：问那个宰相还是丞相最后什么结局。
+- **发言人3**：没看，只看了一点。
+- **发言人4**：西门庆一直换老婆，问潘金莲属于啥。
+- **发言人3**：西门庆有好像十个老婆，有的老婆特别懦弱，潘金莲属于很有心机、比较强势的那一种。
+- **发言人4**：潘金莲前面应该还是差不多，武大郎也是死在潘金莲手下的。
+- **发言人3**：记得西门庆有一个老婆生病了要去看和尚，不去治病，信这个，回来死了；那里面佛教也可黑了，收灯油钱。
+- **发言人2**：《金瓶梅》和《水浒传》是同一时期（北宋）真实发生的一些事情。
+- **发言人3**：《金瓶梅》不写起义章节，就是西门庆这个小人物的发展史。
 ## 《西游记》及其他讨论
-- **发言人1**：西游记里如来佛祖说「区区收了300两黄金」——天庭派人帮一个国家，帮完回来如来嫌收得少。
-- **发言人2**：西游记里佛教虚伪的例子——孙悟空和唐僧单独取经时寄宿寺院，住持有很多袈裟，觊觎唐僧袈裟，后来引火把自己烧死了。
-- **发言人3**：红楼梦没有明确朝代，是一个写得很虚的故事；作者是那个时代的人，映射那个时代。
-- **发言人2**：水浒和金瓶梅是北宋时期，与红楼梦不同；三国、水浒都有明确历史人物和时间线，与真实事件大致相同。
-- **发言人2**：提到孙权二宫之争——太子孙登、鲁王孙霸之争，不同大臣支持不同儿子；孙权老婆王夫人有心机，和女儿孙鲁班一起反杀，把东吴政局搅得一团糟。
+- **发言人1**：《西游记》里如来佛祖说「区区收了300两黄金」，体现佛教虚伪。
+- **发言人2**：记得《西游记》里佛教虚伪一个是狮驼岭，另一个是孙悟空和唐僧单独取经时寄宿寺院，住持有很多袈裟，贪图唐僧袈裟，后来引火把自己烧死了。
+- **发言人4**：提到黑神话游戏里的boss。
+- **发言人1**：还有金齿蟑螂。
+- **发言人2**：问《红楼梦》在历史上有没有真实发生这些历史事件。
+- **发言人3**：《红楼梦》开头就是湖边漫步，是虚构故事，不像三国、水浒有明确历史人物和时间线。
+- **发言人2**：三国、水浒、金瓶梅都是同时期真实发生的事情，问《红楼梦》是不是单独的故事线。
+- **发言人3**：不是一个朝代，《红楼梦》是明清时期，金瓶梅和水浒是北宋时期。
 # 共识形成
-- **一致意见**：与会者普遍认可《红楼梦》存在官场暗线，四大家族兴衰与官场地位相关，如王熙凤地位与其兄长官场地位相关；同时认可《金瓶梅》是西门庆这个小人物的发展史，武松报仇未成、被权势打压是故事转向西门庆的关键节点。
-- **倾向性认识**：多数人倾向认为《红楼梦》映射当时时代，有说法称是曹雪芹个人经历，发言人3补充「要不然他写不出来那个那么多的细节」；发言人1提到《红楼梦》当时是禁书，不敢写明朝代。
-- **主要分歧点**：发言人4质疑四大家族人数少，「每家就两家人多一点」，与诗句中「都很牛逼」的形容不符，发言人3未直接回应人数问题，仅以「整体都在走一个下坡路」解释；关于薛宝钗结局，发言人3提到120回版本中她嫁给贾宝玉但贾宝玉出家，有说法称无性婚姻，另有版本称她后来怀孕，发言人1认为「这个应该不至于弄这么狗血」。
-- **关键口径**：发言人1背诵四大家族诗句「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」；发言人1提到《西游记》中如来佛祖说「区区收了300两黄金」。
+- **一致意见**：与会者普遍认可《红楼梦》存在**官场暗线**，四大家族兴衰与官场地位相关，如王熙凤地位与其兄长在官场上的地位相关；发言人3、发言人1、发言人4均认同四大家族整体处于下坡路，对应王朝家族的衰败。
+- **倾向性认识**：关于《红楼梦》朝代背景，发言人3明确表示**无明确朝代、是虚构故事**，发言人4补充作者曹雪芹可能映射当时时代，且《红楼梦》当时是禁书、不敢写明朝代，与会者对此未提出异议。
+- **主要分歧点**：关于薛宝钗结局，发言人3提出120回版本中她嫁给贾宝玉后贾宝玉不久出家，有说法称无性婚姻，另有版本称她后来怀了孩子；发言人1认为「狗血版本不至于」，发言人2质疑孩子是否为贾宝玉的，发言人3回应「那肯定是狗血版本」。
+- **版本差异共识**：发言人1讲述《金瓶梅》中武松报仇线被高官权势压制、未成功，与《水浒传》中直接杀西门庆不同；发言人3认为《金瓶梅》是西门庆这个小人物的发展史，与会者对此说法未提出反对。
 # 待探讨问题与后续
-- **未确认**：《红楼梦》中四大家族是否真的只有少数人，发言人4质疑每家仅两家人多一点，发言人3回应称可能是没看书，书里人可能不少。
-- **未定论**：《金瓶梅》中西门庆的结局在不同版本中是否不同，发言人2询问水浒版与金瓶梅版结局差异，发言人3称金瓶梅版中西门庆是纵欲过度而死，水浒版中则是被武松砍头。
-- **未确认**：《红楼梦》是否映射曹雪芹个人经历，发言人4提到有这种说法，发言人3认为若非亲身经历写不出那么多细节。
-- **待核实**：《金瓶梅》中武松报仇线是否成功，发言人1讲述武松报仇被高官权势打压、被发配，发言人4询问武松报仇线是否存在，发言人3确认有报仇线但未成功。
-- **未确认**：《金瓶梅》中潘金莲在西门庆妻妾中的地位，发言人3称西门庆有约十个老婆，潘金莲属于有心机、强势的类型，发言人4询问潘金莲是否属于强势类型，发言人3表示印象中如此。
-- **待核实**：《金瓶梅》中西门庆一个老婆因迷信和尚而病死的情节，发言人3提及该细节，发言人4表示细节记不清。
-- **未确认**：《西游记》中如来佛祖收300两黄金的章节出处，发言人1提及该情节但忘记具体章节，发言人2询问后未得到明确答复。
-- **待核实**：《西游记》中寺院住持贪唐僧袈裟引火自焚的情节，发言人2提及但表示记不清细节，发言人3推测可能看的是电视剧版本。
-- **未确认**：《红楼梦》中薛宝钗的结局版本，发言人3提到120回版本中她嫁给贾宝玉但贾宝玉出家，有说法称无性婚姻，另有版本称她后来怀孕，发言人2询问孩子是否为贾宝玉的，发言人3称那是狗血版本。
-- **未定论**：《金瓶梅》与《水浒传》的关系，发言人2询问西门庆与宋江是否有交集，发言人3认为应该不会写但丞相是同一个；发言人2询问宋江起义是否成功，未获明确回答。
-- **未确认**：《红楼梦》的历史背景，发言人3称其没有明确朝代、是虚构故事，发言人4认为作者是那个时代的人、映射当时时代，发言人1提到《红楼梦》当时是禁书、不敢写明朝代。
-- **待核实**：东吴二宫之争中王夫人与孙鲁班搅乱政局的说法，发言人2提及该历史事件并询问大家了解程度，未获回应。</t>
+- **未确认**：《红楼梦》中四大家族是否真的只有少数人，发言人4质疑四大家族每家只登场两家人左右，多数家族仅知典型人物，发言人3回应称薛宝钗家是做生意的、有钱但无官场靠山，发言人1补充护官符诗句后，发言人4仍认为「说都很牛逼，就感觉没什么厉害人家」。
+- **待核实**：《金瓶梅》中西门庆的结局在不同版本中具体如何，发言人2询问后，发言人1称水浒传版本中脑袋被砍，发言人3提到金瓶梅版本中「终于过度死」（语音识别存疑），但未确认具体细节。
+- **未定论**：《红楼梦》是否映射曹雪芹个人经历，发言人4提出「有这种说法不知道您知道」，发言人3以「要不然他写不出来那个那么多的细节」支持该说法，但未达成一致。
+- **未确认**：《金瓶梅》中潘金莲是否属于强势有心机类型，发言人3称「应该算是比较强势的」，发言人4表示认同，但未展开核实。
+- **待核实**：《金瓶梅》中西门庆一个老婆因迷信和尚、不去治病而死的情节，发言人3提出后，发言人4回应「不知道耶细节记不清」。
+- **未确认**：《西游记》中如来佛祖收300两黄金的情节出自哪一章节，发言人1称「好像是最后一集吧」，发言人2追问后未获确认。
+- **未定论**：《金瓶梅》与《水浒传》是否为同一时期真实发生事件，发言人2提出「水浒和金瓶梅也是同时期真实发生的一些事情，对不对」，发言人3未直接确认，仅说明《金瓶梅》是西门庆这个小人物的发展史。
+- **未确认**：《金瓶梅》中西门庆与宋江等人有无交集，发言人2提问后，发言人1称「理亏不知道了」，发言人3推测「应该不会写」，未达成一致。
+- **未确认**：西门庆的十个老婆中除潘金莲外其他人物细节，发言人3仅提及「有的老婆就特别的懦弱」，未展开。
+- **后续约定**：会议因时间关系暂停，发言人1提出「咱们时间差不多了咱们再起一条」，发言人2询问「下一个场景是啥你接」，但未明确下次讨论的具体主题或分工。</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>45.2</v>
+        <v>47.7</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5893/3343</t>
+          <t>5893/3622</t>
         </is>
       </c>
     </row>
@@ -15234,48 +15273,43 @@
       <c r="C43" t="inlineStr">
         <is>
           <t># 全文摘要
-会议为多人自由闲聊，参与者共六位发言人，未明确机构与主办方。前半段围绕个人阅读与综艺观看展开，发言人1提到反复阅读《红楼梦》多次，发言人2与发言人4表示不怎么看小说、更常看短剧和综艺；随后讨论《种地吧》与《克拉克森的农场》两部种地综艺，并谈及专业背景（发言人2为俄语专业但未从事相关职业，发言人1学数学与统计，发言人4学软件工程）。后半段发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法，但发言人5表示不懂，讨论未深入，因设备与人员安排中断。以分享为主，未形成明确结论。
+本次会议为多人参与的闲聊式交流，参与者包括发言人1至发言人6，无明确主办方或正式议程。会议围绕个人兴趣与背景展开，覆盖小说阅读、综艺观看、专业背景及生活话题等板块，具体涉及《红楼梦》阅读体会、《种地吧》与《克拉克森的农场》等综艺内容、俄语与数学统计等专业背景，以及洗发水使用习惯。后半段发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法，但参与者均表示了解有限，话题未深入。会议以分享为主，未形成明确结论。
 # 分段速览
-## 00:00:02-00:05:32 闲聊：阅读与综艺
-会议开场为自由闲聊。发言人1询问在场者是否看小说，发言人2表示不怎么看小说、更常刷短剧，发言人4也认同。发言人1提到自己反复阅读《红楼梦》多次，最初高中时读不太懂，反复读后才觉得有意思。话题随后转向综艺，发言人2和发言人4表示看电视剧和综艺较多，偏好娱乐类、旅游类、户外类及做饭类内容。发言人1介绍《种地吧》综艺，参与者为十个男生，走偶像路线但选择小众的种地题材，录制周期约半年、几乎24小时录制，十人后来组成组合并开演唱会。发言人1还提到英国种地综艺《克拉克森的农场》。
-## 00:05:32-00:08:15 闲聊：农业项目与专业背景
-发言人1继续介绍《种地吧》参与者成立农业公司尝试新型农业，种植小月季和水培蔬菜，有项目盈利也有项目亏损，参与者是实际股东、每人出资，但个人主要收入仍来自综艺。发言人1指出农业门槛较高，种月季需请专人照看水土。随后话题转向专业背景：发言人2是俄语专业但就业时未从事相关工作，称五六年不用已遗忘；发言人1之前学数学、后来学统计；发言人4学软件工程，属工科。
-## 00:08:15-00:12:43 闲聊：护发话题与人员安排
-发言人2称赞发言人4头发多，引发洗发水话题。发言人4表示换着用多种洗发水，目前囤有三种，称换用后头发没那么容易油了，但记不清所用品牌。发言人2询问是否有推荐，发言人4表示稍后找订单告知。随后发言人1结束录制，发言人5接手安排后续录制，涉及中英混播、八爪鱼、金融等人员与设备协调，现场出现人员调度与会议室安排，发言人2表示「不该来这个」。
-## 00:12:43-00:13:02 日本现代化转型讨论
-发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法，并指出发言人5在日本上学、应是主场。发言人5表示对日本现代化转型话题不懂。讨论因设备与人员安排中断，未深入展开。
+## 00:00:02-00:05:32 个人兴趣闲聊
+发言人1询问大家是否看小说，发言人2表示不看小说、主要刷短剧，发言人1提到自己多次阅读《红楼梦》，高中时作为推荐读物最初读不懂，反复读后发现有趣。话题转向综艺，发言人2和发言人4表示主要看电视剧和娱乐综艺。发言人1介绍《种地吧》综艺，十个男生录制半年、几乎24小时录制，成立农业公司，种植小月季和水培蔬菜，项目有亏有盈；还提到英国综艺《克拉克森的农场》。讨论中涉及节目录制周期、收益来源及农业门槛等话题。
+## 00:05:32-00:10:22 专业背景与生活话题
+发言人2为俄语专业，但就业未从事俄语相关工作，因五六年不用已遗忘；发言人1学数学和统计，发言人4学软件工程。随后聊到洗发水使用习惯，发言人4表示换用多种洗发水，认为换着用对头发好，目前囤有三种，并提到用后头发不易出油。
+## 00:10:22-00:13:02 日本现代化转型话题
+发言人5与发言人6接续录制，发言人6提议讨论日本现代化转型，涉及明治维新和和平宪法，但发言人5表示不懂，发言人6也自认不了解，话题未深入，因其他事务中断。
 # 要点梳理
-## 个人阅读与综艺观看
-- **发言人1**：反复阅读《红楼梦》多次，高中初次阅读时不太能读懂，反复读后才觉得有意思。
-- **发言人2**：不怎么看小说，刷短剧更多；平时看电视剧和综艺多一点。
-- **发言人4**：不怎么看小说，看综艺多一点，娱乐类为主，烧脑类看得少。
-- **发言人1**：介绍《种地吧》综艺，参与者为十个男生，走偶像路线但选择小众路线，大部分搞音乐，后来组成组合并开演唱会。
-- **发言人1**：介绍《种地吧》录制情况，几乎24小时录制，一录半年，视频素材特别多。
-- **发言人1**：提到《种地吧》参与者成立农业公司，尝试创业发展新型农业；项目有亏有盈，参与者是实际股东，每人掏钱。
-- **发言人1**：提到《种地吧》种植小月季和水培蔬菜，月季需请专人看水和土，外行人很难做；有一个鱼塘但未认真经营。
-- **发言人1**：提到英国种地综艺《克拉克森的农场》。
-- **发言人1**：提到近期三农主题内容较多，挺多人喜欢看。
-## 专业背景与职业
-- **发言人2**：俄语专业，就业时未从事俄语相关工作，五六年没用已遗忘。
-- **发言人2**：提到康鹏曾科普俄罗斯人贸易相关信息，称其生意内部消化较多、对外营销较少，不怎么外传。
-- **发言人1**：之前学数学，后来学统计，一直是理科生。
-- **发言人4**：理科生，学软件工程，属于工科。
-## 洗发水话题
-- **发言人4**：洗发水换着用，家里囤有三种轮着用；之前头发容易油或痒，换用后没那么容易油了。
-- **发言人4**：未使用海飞丝，所用品牌不认识、叫不上名字，答应之后找订单告诉发言人2。
+## 个人兴趣与背景闲聊
+- **小说阅读**：发言人1多次阅读《红楼梦》，高中时作为推荐读物，最初读不太懂，反复读后发现有意思；发言人2不看小说，主要刷短剧。
+- **综艺观看**：发言人2和发言人4主要看电视剧和综艺，以娱乐综艺为主，烧脑类看得少；发言人4偏好旅游类、户外类综艺，发言人2提到做饭类综艺。
+- **《种地吧》介绍**：发言人1介绍该综艺，十个男生录制半年，几乎24小时录制，视频素材多；十人多为搞音乐出身，录完后组成组合，粉丝较多。
+- **《种地吧》农业经营**：十人成立农业公司，尝试创业发展新型农业；种植小月季和水培蔬菜，有专门人员帮看水和土；项目有亏有盈，十人作为实际股东每人掏钱；有鱼塘但未认真经营；个人挣钱主要靠综艺，节目内以农业主题讲农业如何挣钱。
+- **《克拉克森的农场》**：发言人1提到英国种地题材综艺，认为好看。
+- **三农主题趋势**：发言人1提到最近三农主题内容较多，挺多人喜欢看。
+- **专业背景**：发言人2为俄语专业，就业未从事俄语相关工作，因56年没用已遗忘；发言人1学数学和统计，发言人4学软件工程（工科）。
+- **俄语贸易话题**：发言人2提到北方可能用到俄语做贸易，康鹏曾科普俄罗斯人贸易相关信息，称其生意内部消化较多、对外营销较少，不怎么外传。
+- **洗发水使用**：发言人4换用多种洗发水，认为换着用对头发好，目前囤有三种；发言人2听说洗发水换着用对头发好，询问推荐，发言人4表示找到订单后告知牌子。
 ## 日本现代化转型讨论
-- **发言人6**：提议讨论日本现代化转型，涉及明治维新与和平宪法。
-- **发言人5**：表示对日本现代化转型话题不懂。
-- **发言人6**：提到发言人5在日本上学，称其是主场。
-- **发言人5**：因设备与人员安排（八爪鱼、金融相关事务），讨论未深入即中断。</t>
+- **议题提出**：发言人6提议讨论日本现代化转型，涉及明治维新和和平宪法。
+- **参与方回应**：发言人5表示对日本现代化转型话题不懂；发言人6自认对日本话题不太懂。
+- **讨论中断**：话题未深入，因其他事务（录音安排、会议室使用等）中断。
+## 结论与决定
+- 会议以闲聊为主，未形成明确结论或决定。
+## 行动项与分工
+- 发言人4承诺找到洗发水订单后告知发言人2所用牌子，未明确时限。
+## 待确认与风险
+- 日本现代化转型话题因发言人5和发言人6均表示不了解而未深入，未达成讨论结果。</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>27.7</v>
+        <v>29</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5310/1910</t>
+          <t>5310/1618</t>
         </is>
       </c>
     </row>
@@ -15432,96 +15466,101 @@
       <c r="C44" t="inlineStr">
         <is>
           <t># 讲座概况
-主讲人系统梳理了朝鲜半岛从分裂到统一再到二战后分裂的历史脉络，重点讲解朝鲜战争爆发背景、主要战役、停战协定及战后影响，并现场解答听众关于朝韩现状、旅游、军队战斗力、中美关系等提问。讲座面向对朝鲜战争历史及半岛现状感兴趣的听众，围绕朝鲜半岛历史与朝鲜战争、朝鲜旅游与现状、半岛分裂原因与统一展望、韩军表现、抗美援朝决策与中美关系、中俄朝关系与图们江出海口等板块展开。核心判断包括：朝鲜战争奠定中国强国地位，美国在越南战争中未敢越过北纬十七度线；朝韩仅名义停战，三八线悲剧延续至今；韩军战斗力在1952年前弱、之后不可小视。关键锚点：1950年6月朝鲜战争爆发、1953年7月27日停战协定、1950年10月19日志愿军跨过鸭绿江。对听众而言，有助于理解朝鲜半岛问题的历史根源与当前东北亚格局。
+主讲人（发言人1）以朝鲜半岛历史为线索，系统讲解朝鲜战争从爆发到停战的完整脉络，并现场解答听众关于朝韩现状、军队战斗力、中美关系等疑问。讲座面向对朝鲜战争及半岛局势感兴趣的听众，围绕朝鲜半岛分裂与统一、朝鲜战争进程与各方称谓、战后影响与朝韩现状、抗美援朝决策原因等板块展开。核心判断包括：朝鲜战争奠定中国强国地位，美国在越南战争中未敢越过北纬十七度线；朝韩仅名义停战，三八线悲剧延续至今；若朝韩统一，大概率是韩国兼并朝鲜，但可能成为东北亚不稳定因素。关键锚点：1950年6月战争爆发、1953年7月27日停战协定、三八线及金刚山旅游景点。对听众而言，有助于理解朝鲜半岛问题的历史根源与当前格局。主讲人姓名未提及。
 # 核心观点与论证
 ## 朝鲜战争爆发背景与各方称谓
-- **三八线形成**：1945年二战结束、日本投降后，美苏军队分别开进朝鲜半岛南北，以北纬38度为基准形成三八线；此前半岛历经高丽、百济、新罗从分裂到统一，二战后再次分裂。
-- **苏联鼓动朝鲜南进**：1949年新中国宣布废除列强在华一切租界及特权，含苏联在东北的中长铁路及大连、旅顺特区利益；苏联不甘心，鼓动朝鲜进攻韩国，希望以仁川或釜山替代旅顺、大连地位，继续在亚洲发挥影响力。
-- **战争爆发与各方称谓**：1950年6月北朝鲜军队率先越过三八线南攻，朝鲜战争爆发；朝鲜称`祖国统一解放战争`，中国称`抗美援朝`，韩国称`625事件`，美国及西方称`朝鲜战争`或`韩战`（韩战主要为台湾地区称谓）。
-- **初期战况与仁川登陆**：战争开始后朝鲜人民军从三八线打到洛东江环形防御圈（今大邱至釜山一带）；1950年9月15日美军仁川登陆成功，将深入韩境的朝鲜人民军分割包围、逐次歼灭，收复三八线以南领土。
+- **分裂起点**：1945年第二次世界大战结束、日本投降后，美国和苏联军队分别开进朝鲜半岛北部和南部，以北纬38度为基准形成三八线。
+- **苏联鼓动开战**：1949年新中国宣布废除列强在华一切租界及特权，包含苏联在东北的中长铁路及大连、旅顺特区利益；苏联不甘心，鼓动朝鲜进攻韩国，希望以仁川或釜山类城市替代旅顺、大连地位，继续在亚洲发挥影响力。
+- **战争爆发与称谓**：1950年6月北朝鲜军队率先越过三八线南进，朝鲜战争爆发；各方称谓不同——朝鲜称`祖国统一解放战争`，中国称`抗美援朝`，韩国称`625事件`，美国及西方国家称`朝鲜战争`或`韩战`（台湾地区称谓）。
+- **初期战况**：战争开始后朝鲜人民军从三八线一路打到洛东江环形防御圈（今大邱到釜山一带）；1950年9月15日美军在仁川登陆成功，将深入韩国境内的朝鲜人民军分割包围、逐次歼灭，收复三八线以南领土。
 ## 中国出兵与主要战役进程
-- **中国出兵决策**：联合国军由美军主导、16国共同出兵，总司令麦克阿瑟欲扩大战果吞并整个北朝鲜；因朝鲜半岛对中国呈`唇亡齿寒`状态，美军越过三八线后，中国决定以志愿军形式出兵。
-- **入朝时间线**：1950年10月19日志愿军跨过鸭绿江，10月25日与韩国军队首次交火，11月5日第一次战役结束；此后相继进行第二次战役（含长津湖战役）、第三次战役。
-- **推进至三七线**：第三次战役越过三八线，占领汉城（今首尔）及仁川、水原一带，将战线推进至北纬37度；后期美军反攻，双方在三八线与三七线之间鏖战。
-- **第五次战役与停战**：第五次战役为最后一次大规模战役，结束后双方在三八线基础上互有攻防；西部中朝方面占领开城、延安半岛、望京半岛，东部美军占领襄阳、金刚山地区（金刚山今为韩国著名旅游景点）。
-- **停战协定**：1953年7月27日双方正式达成停战协定并延续至今，朝韩仅名义上停战、未实现真正和平；三八线非军事区（DMZ）与金刚山现为旅游景点。
+- **出兵决策**：美军以联合国军身份参战（共十六国共同出兵），联合国军总司令麦克阿瑟想扩大战果吞并整个北朝鲜，此举招致中国强烈不满——朝鲜半岛对中国是`唇亡齿寒`状态。
+- **入朝时间线**：1950年10月19日志愿军跨过鸭绿江；10月25日与韩国军队第一次交火；11月5日第一次战役顺利结束。
+- **后续战役**：第二次战役即长津湖战役（国内影视作品多有宣传）；第三次战役越过三八线，占领汉城（今首尔）、仁川、水源等地，推进至三七线（北纬37度一带）。
+- **停战与边界**：第五次战役（最后一次大规模战役）后双方沿三八线互有攻防；1953年7月27日正式达成停战协定，朝韩仅名义停战、未实现真正和平；西部中朝占领开城、延安半岛和望京半岛，东部美军占领襄阳和金刚山地区（金刚山现为韩国著名旅游景点，另有DMZ三八线非军事区旅游景点）。
 ## 朝鲜战争的历史影响
-- **奠定中国强国地位**：从中国角度，战争奠定强国地位，美国再不敢小瞧中国；1967年越南战争时期中国警告美国不得越过北纬十七度线（南越与北越边境线），否则中国必将出兵越南，美国未敢逾越。
-- **美国称被遗忘的战争**：联合国军最后一任司令官马克·克拉克承认，他是美国历史上第一位在未取得胜利情况下签署停战协议的司令官；美国称此战为`被遗忘的战争`。
-- **朝韩两败俱伤**：伤害最深的实为朝鲜和韩国——双方本是一脉相承的血肉同胞，却分裂成两个国家，三八线悲剧延续至今。
-## 朝鲜半岛分裂原因与统一展望
-- **美苏冷战布局**：美国在三八线以南单独建立韩国，是为保护日本免遭苏联及共产主义势力影响；苏联则需在亚洲建立卫星附属国，故扶植北朝鲜独立建国，奉行对苏马首是瞻政策。
-- **统一计划落空**：最初计划像奥地利一样在不同占领区受降后举行普选、建立统一民选政府；但美苏关系急转直下，所扶植领导人各有心思，因意识形态不同最终建立两个国家，成为朝鲜战争爆发缘由。
-- **若美国未下场的假设**：若朝鲜战争爆发时美国未救援韩国，今日朝鲜可能成为苏联卫星国，既是牵制中国的钉子，也是威胁美国在亚洲（尤其日本）的定时炸弹。
-- **统一前景判断**：朝韩若统一大概率是韩国兼并朝鲜——经济影响和综合实力摆在那里；但北方有充足优质兵源及核武器、导弹等尖端武器，统一后对整个东北亚都是不稳定定时炸弹。
-- **越南类比**：越南统一第二年即进攻柬埔寨和泰国，中国被迫于1979年出兵发动对越自卫反击战；越南尚且如此，朝鲜半岛统一后局势更不可控。
-## 韩军战斗力评价
-- **初期表现差**：1950年6月25日战争爆发后，韩军因瞎指挥差点被朝鲜团灭；7月10日以后南部地面战斗主要由美军与朝鲜人民军进行，韩军初期只负责`冲人头`角色。
-- **1952年转折**：1952年后美军重新整训韩军，韩军才形成基本战斗力；此前对美军而言类似`猪队友`，志愿军与美军占不到便宜时常从韩军战线突击，美军每次兵败多由韩军战线崩溃引起。
-- **第五次战役溃败**：第五次战役中志愿军从朝鲜半岛东部对韩军形成反包围突击，打崩其前线；美国人在韩国领土上撤销了韩国第三军团。
-- **军队构成与文化**：韩军军官主体是二战时期日本扶植的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁强征的农村青年；贯彻昭和日军武士道精神，老兵欺负新兵、军队霸凌事件延续至今，被视为旧日军部队的延伸。
-## 抗美援朝而非收复台湾的决策
-- **海军实力不足**：台湾海峡距离约100公里，中共刚建国没有相应海军实力，无法进行解放台湾的战斗。
-- **美国介入台海**：1950年朝鲜战争爆发后，美国参众两院视其为共产主义世界对自由世界的全面进攻，将台湾和韩国共同纳入亚太保护圈；美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。
-- **唇亡齿寒的必然选择**：美军越过三八线向中朝边境进发，触动中国敏感神经，即便不愿与美国爆发全面战争也不得不打；既然海上无法战斗，就在陆地上战斗——长津湖和上甘岭两场战役接连让美军惨败，至今仍是美国人挥之不去的梦魇。
-## 当前美朝关系与中俄朝关系
-- **美国忌惮中俄**：美国因惧怕朝鲜背后的中国和俄罗斯而未主动进攻朝鲜——朝鲜战争时中国出动志愿军、苏联提供空军掩护和武器后勤支持，联手把美国打回三八线以南；美国不敢再次挑起半岛武装冲突。
-- **朝鲜不敢贸然动武**：金家担心江山一旦贸然发动战争会被重新颠覆，故也不敢发动战争。
-- **图们江出海口问题**：中俄朝关系`各怀鬼胎`，图们江出海口问题至今未解决——图们江是俄罗斯与朝鲜的界江、通往日本海的出海口，但俄朝建了一座小桥，大船无法通行；俄朝都不希望中国过分强大，不愿让出出海口。
+- **奠定中国强国地位**：朝鲜战争后美国再不敢小瞧中国；1967年越南战争时期中国警告美国绝对不允许越过北纬十七度线（当时南越与北越边境线），否则中国必将出兵越南，美国在越战期间未敢越过该线。
+- **美国视角**：这场战争在美国被称为`被遗忘的战争`；美军最后一任司令官马克·克拉克承认，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。
+- **朝韩代价**：伤害最深的还是朝鲜和韩国——本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
+## 朝韩分裂的历史渊源
+- **美苏各自诉求**：美国在南方单独建立韩国，是为保护日本免遭苏联及共产主义势力影响、形成缓冲区；苏联需要在亚洲建立卫星附属国，故在北方扶植北朝鲜，奉行对苏联马首是瞻的指示。
+- **统一设想落空**：最初设想是在不同占领区受降后像奥地利那样举行普选、建立统一民选政府；但美苏关系恶化急转直下，所扶植的领导人各有心思，因意识形态不同最终建立两个国家，这也是朝鲜战争爆发的缘由。
+## 朝韩现状与统一前景
+- **美国态度**：美国因惧怕朝鲜背后的中国和俄罗斯而未主动进攻朝鲜——朝鲜战争时中国出动志愿军把美军打回去，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南；朝鲜金家也担心贸然发动战争后江山被颠覆，故双方维持现状。
+- **统一前景判断**：若朝韩统一，大概率是韩国兼并朝鲜——经济影响和综合实力摆在那儿；但北方有充足优质兵源及核武器、导弹等尖端武器，统一后对整个东北亚地区都是不稳定定时炸弹。
+- **越南类比**：越南统一时宣布继承法国在中南半岛所有地盘和疆域，统一第二年就进攻柬埔寨和泰国，逼得中国1979年出兵对越南发动自卫反击战；越南尚且如此，朝鲜半岛统一后局势更加不可控。
+## 韩国军队战斗力评价
+- **1952年前表现**：战争初期韩军瞎指挥，差点被朝鲜团灭；1950年6月25日战争爆发后，从7月10日起朝鲜南部地面战斗主要是美军与朝鲜人民军进行，韩军只负责`冲人头`角色；志愿军与美军占不到便宜时都从韩军战线突击，美军每次兵败都由韩军战线崩溃引起。
+- **第五次战役崩溃**：志愿军从朝鲜半岛东部韩军战线形成反包围突击，把整个韩军前线打崩，美国把韩国第三军团全部撤销——美国人在韩国领土上撤销了韩国军队。
+- **1952年后整训**：1952年后美国重新整军训练备战，韩军才形成基本战斗力；韩军军官主体是二战时期日本人扶植的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁强征的农村青年。
+- **军队传统延续**：韩军从朝鲜战争成军至今一直贯彻二战时期昭和日军的武士道精神管理体制，老兵欺负新兵、军队霸凌事件蔓延至今，是充满昭和军国主义思想余孽的旧日军部队延伸。
+## 抗美援朝而非收复台湾的决策逻辑
+- **海军实力不足**：台湾与大陆之间海峡距离约100公里，中共刚建国没有相应海军实力，无法进行解放台湾的战斗。
+- **美国亚太布局**：1950年朝鲜战争爆发后，美国参众两院普遍视为共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈——陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。
+- **唇亡齿寒考量**：美军越过三八线向朝鲜及中朝边境进发，触动中国敏感神经，`唇亡齿寒`概念深入人心；即便不愿与美国爆发全面战争，又不得不打——台湾问题已让中国被动，朝鲜半岛要争取战略主动。
+- **陆地作战优势**：解放军陆军很强，海上无法战斗就在陆地战斗；长津湖和上甘岭两场战役接连让美军惨败，至今是美国人挥之不去的梦魇。
+## 朝鲜旅游与信息封锁
+- **入境限制**：进入朝鲜境内第一件事是搜手机检查；没有无线网和网络，只有平壤有自己的网络运营商，状态类似中国八九十年代；手机很落后很慢，国际漫游和网络非常贵。
+- **参观内容**：参观`伟大的今日成员在的感召之下`的各种主体思想和社会主义辉煌建设成就，类似以前文革时期无产阶级高于一切的思想，活在异次元世界当中。
+- **信息封锁原因**：普通人连电脑和5G手机都用不起，局域网都很有限；外部有韩国用韩剧作为意识形态宣传武器，老百姓知道真相后会颠覆政权——否则不会有那么多朝鲜老百姓吃不饱肚子还往韩国跑（脱北者），鲜有韩国人去朝鲜。
+- **传单与连带责任**：韩国用飞机向朝鲜发传单、发韩国文化内容；朝鲜严防死守，谁家被发现私藏就要被追究连带责任。
+## 朝鲜半岛文明与中朝关系
+- **文明渊源**：朝鲜半岛文明是中华文明衍生物，约3500年历史，最早可追溯到商周时期形成初步文明；长期是中华文化圈的中原附属国，直到甲午战争清朝战败后才彻底脱离与中国隶属关系，成立大韩帝国，后与日本合并，二战后复国又被分裂。
+- **图们江出海口问题**：中国、俄罗斯、朝鲜关系`各怀鬼胎`；图们江是俄罗斯和朝鲜的界江，是日本海出海口，国际水域航道可通行，但俄罗斯和朝鲜建了一座小桥，大船无法通过——两国都不希望中国过分强大，把出海口封死。
 # 金句总结
-&gt; 唇亡齿寒。
-- 讲到美军越过三八线、进犯中朝边境时，说明中国决定出兵朝鲜的原因。
-&gt; 美国再也不敢小瞧我们了。
-- 总结朝鲜战争对中国国际地位的影响，并引出越南战争时期中国警告美国不得越过北纬十七度线。
-&gt; 他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。
-- 引用联合国军最后一任司令官马克·克拉克的自述，说明美国对朝鲜战争的定性。
-&gt; 伤害最深的其实还是朝鲜和韩国，毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家。
-- 评价朝鲜战争对朝韩两国的伤害，指出三八线悲剧延续至今。
-&gt; 各怀鬼胎。
-- 回答中国、俄罗斯、朝鲜三国关系现状时，指出三国各有自身利益考量。
-&gt; 既然海上没办法进行战斗，那就只能在陆地上进行战斗。
-- 解释新中国为何选择抗美援朝而非解放台湾，强调当时解放军陆军优势与海军短板。
-&gt; 长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。
-- 总结抗美援朝中两场关键战役对美军的震慑作用。
+&gt; “美国再也不敢小瞧我们了，导致在一九六七年的越南战争时期，中国这边向美国发出的警告，绝对不允许越过北纬十七度线。”
+- 背景：回答听众关于朝鲜战争改变大小的提问，论及战争对中国国际地位的奠定作用。
+&gt; “他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。”
+- 背景：讲述美国称朝鲜战争为“被遗忘的战争”，引用联合国军末任司令官马克·克拉克的自我承认。
+&gt; “伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家，并且这样的三八线的悲剧延续至今。”
+- 背景：总结朝鲜战争对朝韩两方的深层伤害，强调同族分裂的悲剧延续至今。
+&gt; “朝鲜半岛对于中国的意义来说，就是一个唇亡齿寒的一个状态。”
+- 背景：解释美军越过三八线后中国决定出兵抗美援朝的战略考量。
+&gt; “既然海上没办法进行战斗，那就只能在陆地上进行战斗。”
+- 背景：回答为何选择抗美援朝而非收复台湾，说明当时解放军海军实力不足、陆军强大的现实选择。
+&gt; “俄罗斯和朝鲜都不希望咱们过分强大，然后不想过多依附于我们，所以说在那个图们江出海口给封死了。”
+- 背景：回答中俄朝关系现状，指出图们江出海口被俄朝建桥封死、阻碍中国出海的问题。
+&gt; “今日朝韩如果统一的话，那对于整个东北亚地区来说，都是一颗不稳定的定时炸弹。”
+- 背景：畅想朝韩统一可能性时，类比越南统一后入侵柬埔寨，警示统一后局势不可控。
+&gt; “在一九五二年之前我不敢恭维，在一九五二年之后还是不可小视。”
+- 背景：评价韩国军队战斗力，指出1952年前屡战屡败、经美军整训后才形成基本战斗力。
 # Q&amp;A 环节
-**听众**：这场战争开始和结束时，韩国和朝鲜的势力有很大差别吗？战争的改变大吗？
-**主讲人**：从中国角度说，奠定了我们强国地位，美国再不敢小瞧我们，导致1967年越南战争时中国警告美国绝不允许越过北纬十七度线，美国未敢越线。这场战役在美国被称为被遗忘的战争，联合国军最后一任司令官克拉克承认他是美国历史上第一次在未取得胜利的情况下签署停战协定的司令官。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
+**听众**：这场战争开始和结束时，韩国和朝鲜的势力有很大差别吗？战争带来的改变大吗？
+**主讲人**：从中国角度说，奠定了我们强国的地位，美国再不敢小瞧我们，导致1967年越南战争时期中国警告美国不得越过北纬十七度线，美国果然未敢越过。这场战争在美国被称为“被遗忘的战争”，最后一任司令官马克·克拉克承认他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
 **听众**：现在越南还分南北吗？
-**主讲人**：没有，越南是统一的，美国最终放弃了南越，北越趁机会把南越统一了。
+**主讲人**：没有，越南是统一的。美国最终放弃了南越，北越趁机会把南越统一了。
 **听众**：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
-**主讲人**：当然是韩国更好玩。朝鲜旅游没有人身自由，入境第一件事搜手机检查，没有无线网，只有平壤有他们自己的网络运营商，类似咱们国家八九十年代的状态，手机很落后很慢，国际漫游和网络非常贵。那几天就是参观主体思想和社会主义辉煌建设成就，类似以前文革时期那种无产阶级高于一切的思想，活在异次元的世界当中。
+**主讲人**：当然是韩国更好玩。朝鲜旅游限制很严，入境第一件事搜手机检查，没有无线网，只有平壤有他们自己的网络运营商，类似咱们国家八九十年代的状态，手机很落后很慢，国际漫游和网络非常贵。那几天就是参观主体思想和社会主义辉煌建设成就，类似以前文革时期那种无产阶级高于一切的思想，活在异次元的世界当中。
 **听众**：他们普通人可以上网吗？
-**主讲人**：普通人不能上网，局域网都很有限，普通人连电脑和5G手机都用不起。因为外部有韩国，韩国用韩剧作为意识形态宣传武器，老百姓知道真相后会颠覆政权，否则为什么那么多朝鲜老百姓吃不饱肚子还往韩国跑？鲜有韩国人会去朝鲜，就是脱北者。
-**听众**：他们有拿飞机往朝鲜发传单，发韩国文化那种图，文化入侵？
-**主讲人**：有的，朝鲜严防，只要被发现谁家私藏，肯定要追究连带责任。
+**主讲人**：普通人不能上网，局域网都很有限，普通人连电脑和5G手机都用不起。主要是外部有韩国，光是用韩剧作为意识形态宣传武器，老百姓知道真相后会颠覆政权，所以那么多朝鲜老百姓吃不饱肚子还往韩国跑，鲜有韩国人去朝鲜，这就是脱北者现象。
+**听众**：他们有用飞机往朝鲜发传单、发韩国文化那些东西吗？
+**主讲人**：有的，朝鲜严防，只要被发现谁家私藏，肯定要连带责任追究。
 **听众**：朝鲜那边有啥好玩的？
-**主讲人**：也就平壤那边看看志愿军抗美援朝的功绩，还有开城，毕竟是朝鲜半岛三千年古都，特产小人参。
-**听众**：朝鲜有他们古代的文化吗？高丽，还有韩剧里讲朝鲜古代将军什么的。
-**主讲人**：朝鲜半岛文明是中华文明的一个衍生物，文明有3500年历史，最早是商周时期形成初步文明。高丽半岛一直是中华文化圈的一个附属国，一直到甲午战争清朝战败后，朝鲜才彻底脱离和中国的隶属关系，成立大韩帝国，后来跟日本合并，二战后复国又被分裂。
-**听众**：朝鲜是不是和北京或俄罗斯有一个很大的广场？平壤的金日成广场，是以领导人命名吗？
-**主讲人**：对，以领导人来命名，他们大将军、大元帅这样的。
+**主讲人**：也就平壤看看志愿军抗美援朝功绩，还有开城，毕竟是朝鲜半岛三千年古都，特产小人参。整个朝鲜半岛都盛产这玩意儿。
+**听众**：朝鲜有他们古代的文化吗？像高丽，还有韩剧里讲的朝鲜古代将军什么的。
+**主讲人**：朝鲜半岛文明是伴随中华文明的衍生物，文明有3500年历史，最早是商周时期形成初步文明。高丽半岛一直是中华文化圈中原附属国的形式存在，一直到甲午战争清朝战败，朝鲜才彻底脱离与中国隶属关系，成立大韩帝国，后来与日本合并，二战后复国又被分裂成朝鲜和韩国。
+**听众**：朝鲜是不是有像北京或俄罗斯那样很大的广场，就是平壤的金日成广场，是以领导人命名的吗？
+**主讲人**：对，以领导人命名，他们大将军、大元帅这样的。
 **听众**：南北之间的割裂有什么历史渊源？为什么会成为两个政权？
-**主讲人**：一开始美国和苏联都希望在朝鲜半岛建立缓冲区。美国在分出三八线以南单独建立韩国，是为了保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建立卫星附属国，所以宣布北朝鲜独立，奉行对苏联马首是瞻的指示。两边最初诉求本来是在不同占领区受降后，像奥地利那样普选建立统一民选政府，但美苏关系恶化得非常快，所扶植的领导人也各有心思，由于意识形态不同，最终建立了两个不同国家，这也是朝鲜战争爆发的缘由。
-**听众**：当时美国没有打败朝鲜，你觉得现在美国对朝鲜的态度是怎样的？
-**主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争爆发时朝鲜快被美国完全占领，中国出动志愿军帮着朝鲜把美国打回去，苏联也提供了空军掩护和武器后勤支持，中苏联手把美国打回三八线以南。美国比较忌惮，没有主动进攻朝鲜，也没再次挑起半岛武装冲突。朝鲜金家也担心贸然发动战争后江山被颠覆，所以也不敢贸然发动战争。
-**听众**：现在的朝韩对立可以认为是韩国和西方国家在背后支撑，是一个微妙的平衡。如果当时没有形成冷战布局、互相争夺半岛控制权的话，大一统的朝鲜半岛会是什么形态？大号的朝鲜还是平衡的韩朝？
-**主讲人**：如果朝鲜战争爆发时美国没有下场救援韩国，今日朝鲜可能会是苏联卫星国附属之下、用来牵制咱们国家的一颗钉子，也是威胁美国在亚洲尤其是日本的不稳定定时炸弹。现在朝韩要是统一，大概率是韩国兼并朝鲜，毕竟经济影响和综合实力摆在那儿；但北方有充足优质兵源以及核武器和导弹尖端武器，统一后对整个东北亚地区都是一颗不稳定的定时炸弹。当年越南统一时宣布继承法国在中南半岛所有地盘，统一第二年就去进攻柬埔寨和泰国，被逼到79年出兵对越南发动自卫反击战。越南尚且如此，朝鲜半岛统一之后局势更加不可控。
+**主讲人**：一开始美苏都希望在朝鲜半岛建立缓冲区。美国在三八线以南单独建立韩国，是为保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建立卫星附属国，所以在朝鲜北部宣布北朝鲜独立，奉行对苏联马首是瞻的指示。两边最初诉求本来是在不同占领区受降后像奥地利那样普选建立统一民选政府，但美苏关系恶化非常快，所扶植的领导人也各有心思，因意识形态不同最终建立两个国家，这也是朝鲜战争爆发的缘由。
+**听众**：美国没有打败朝鲜，你觉得现在美国对朝鲜的态度是怎样的？
+**主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争时朝鲜快被美国完全占领，中国出动志愿军帮着打回去，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南。美国忌惮这一因素，没有主动进攻朝鲜，也没再挑起半岛武装冲突。朝鲜金家也担心江山一旦贸然发动战争被颠覆，所以也不敢贸然发动战争。
+**听众**：现在的朝韩对立可以认为是韩国和西方国家在背后支撑的微妙平衡吗？如果当时没有冷战布局争夺半岛控制权，大一统的朝鲜半岛会是什么形态？是大号朝鲜还是平衡的韩朝？
+**主讲人**：如果朝鲜战争时美国没下场救援韩国，今日朝鲜可能是苏联卫星国，用来牵制咱们国家的一颗钉子，也是威胁美国在亚洲尤其是日本的定时炸弹。现在朝韩若统一，大概率是韩国兼并朝鲜，毕竟经济和综合实力摆在那儿，北方有充足优质兵源及核武器导弹尖端武器，统一后对整个东北亚都是不稳定定时炸弹。当年越南统一时宣布继承法国在中南半岛所有地盘，第二年就进攻柬埔寨和泰国，被咱们逼到79年出兵对越南自卫反击战。越南尚且如此，朝鲜半岛统一后局势更加不可控。
 **听众**：你感觉现在中国、俄罗斯和朝鲜之间关系怎么样？
-**主讲人**：各怀鬼胎。咱们和朝鲜、俄罗斯的问题主要是图们江出海口问题，到今天还拖着没着落。
-**听众**：什么出海口？
-**主讲人**：图们江是俄罗斯和朝鲜的界江，那个地方是日本海的出海口，在中朝俄边境那块，国际水域航道可以通行，但俄罗斯和朝鲜建了一座小桥，大船没法过去。俄罗斯和朝鲜都不希望咱们过分强大，不想过多依附于我们，所以把图们江出海口封死了，都不想把出海口让给我们。
-**听众**：你觉得朝鲜战争中朝鲜军队和韩国军队有没有发挥什么作用？
-**主讲人**：一开始韩国军队瞎指挥，差点被朝鲜团灭。6月25日战争爆发，7月10日以后南部地面战斗主要是美军和朝鲜人民军打，韩军一开始负责冲人头。差不多1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力。在此之前韩军对美军来说像猪队友，志愿军跟美军占不到便宜时都从韩国军队战线突击，美军每一次兵败都是韩国军队战线崩溃引起的。第五次战役中志愿军从朝鲜半岛东部形成反包围突击，把整个韩国军队前线打崩，美国把韩国第三军团全部撤销，是美国人在韩国领土上把韩国军队给撤销了。韩军战斗力1952年之前我不敢恭维，1952年之后还是不可小视。韩军军官主体是二战时期日本人扶植起来的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁强征的农村青年。韩军从朝鲜战争成军一直到现在，贯彻二战时期昭和日军那套武士道精神管理体制，老兵欺负新兵、军队霸凌事件一直蔓延到今天，是一支充满昭和军国主义思想余孽的旧日军部队延伸。
-**听众**：1950年援朝时中国刚成立，实力不是很强，为什么选择抗美援朝而不是收复台湾？
-**主讲人**：台湾和大陆之间有一道漫长海峡，距离差不多100公里左右。中共刚刚建国，没有相应海军实力。50年朝鲜爆发战争，美国参众两院普遍认为这是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，一来防止解放军解放台湾，二来防止国民党反攻大陆。解放军建军时没有相应海军实力，没办法进行解放台湾的战斗。但美国后期越过三八线向朝鲜及中朝边境进发，触动了咱们的敏感神经，唇亡齿寒概念深入人心，导致即便不愿意和美国爆发全面战争，又不得不进行。台湾那事已经让咱们很被动，朝鲜半岛这场既然要争取战略主动，解放军陆军很强，海上没办法战斗，就只能在陆地上战斗。这也是后来战斗意志的体现，长津湖和上甘岭接连让美军惨败，这两场战役到今天也是美国人挥之不去的梦魇。</t>
+**主讲人**：各怀鬼胎。咱们和朝鲜、俄罗斯的问题主要是图们江出海口，到今天还拖着没着落。图们江是俄罗斯和朝鲜的界江，是日本海出海口，在中朝俄边境那块国际水域航道可以通行，但俄朝建了一座小桥，大船没法过去。俄朝都不希望咱们过分强大，不想过多依附于我们，所以把图们江出海口封死了。
+**听众**：朝鲜战争中朝鲜军队和韩国军队有没有发挥什么作用？
+**主讲人**：一开始韩国军队瞎指挥，差点被朝鲜团灭。6月25号战争爆发，7月10号以后朝鲜南部地面战斗主要是美军和朝鲜人民军打，韩军一开始负责冲人头。差不多1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力。此前韩军对美军有点像猪队友，志愿军跟美军占不到便宜时都从韩国军队战线突击，美军每次兵败都是韩军战线崩溃引起。第五次战役中志愿军从朝鲜半岛东部形成反包围突击，把整个韩军前线打崩，美国把韩国第三军团全部撤销——美国人在韩国领土上把韩国军队撤销了。1952年前韩军战斗力不敢恭维，1952年后不可小视。韩军军官主体是二战时日本人扶植的伪军傀儡部队骨干，士兵类似国民党抓壮丁强征的农村青年，一直贯彻昭和日军武士道精神管理体制，关西兵、老兵欺负新兵，军队霸凌事件蔓延至今，是充满昭和军国主义思想余孽的旧日军部队延伸。
+**听众**：1950年援朝鲜时中国刚成立，实力不强，为什么选择抗美援朝而不是收复台湾？
+**主讲人**：台湾和大陆之间海峡距离差不多100公里，当时中共刚建国没有相应海军实力。50年朝鲜战争爆发，美国参众两院普遍认为这是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾也防国民党反攻大陆。解放军建军时没有海军实力，没办法进行解放台湾战斗。但美军越过三八线向中朝边境进发，触动咱们敏感神经，唇亡齿寒概念深入人心，即便不愿和美国爆发全面战争又不得不打。台湾那事已让咱们很被动，朝鲜半岛既然要争取战略主动，解放军陆军很强，海上没办法战斗就只能在陆地战斗，这也是长津湖和上甘岭接连让美军惨败、到今天仍是美国人挥之不去梦魇的战斗意志体现。</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>69.7</v>
+        <v>68.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7464/6160</t>
+          <t>7464/6622</t>
         </is>
       </c>
     </row>
@@ -15710,49 +15749,52 @@
       <c r="C45" t="inlineStr">
         <is>
           <t># 对话概况
-本次闲聊由发言人1以“出门必带的三样东西是什么”提问开场，五名发言人围绕个人随身物品习惯展开漫谈，话题从必带物品（手机、充电宝、指甲刀、钥匙、皮圈、耳机、工卡等）自然延伸至头发打理与个人形象，再因提及“秋天容易下雨”转入北京降雨与居住安全讨论。主要话题包括：出门必带物品、钥匙与电子锁使用习惯、头发打理与形象偏好、留长发胡子的个人经历、北京降雨季节性与低洼居住风险。倾向与差异方面：多数人认可手机必带，分歧主要在“必要”与“安心”之间——发言人2以指甲刀平替钥匙、上班必带刮胡刀（平均每三天一次，因胡子一天能长几毫米），发言人5则每日带手机、耳机和工卡；关于绑发与披发，发言人1认为散头发更好看，发言人2表示若自己是女生会选择披发，因绑发显得脑袋大。整体以分享为主，未形成明确结论。可作锚点的事例包括：发言人2胡子一天长几毫米、平均每三天带一次刮胡刀上班、发言人2留胡子时曾被误认为新疆少数民族。
+本次闲聊由发言人1以“出门必带的三样东西”提问开场，五名发言人围绕个人随身物品习惯展开漫谈，话题从必带物品延伸到头发打理与个人形象、下雨季节与居住安全等生活琐事，全程以分享个人经验为主，未形成明确结论。主要话题包括：出门必带物品（手机、充电宝、指甲刀、钥匙、皮圈、刮胡刀、耳机、工卡等）、电子锁替代钥匙的便利性、初中男生薅女生头发圈的现象、长发与胡子的打理难度、北京下雨的季节规律及园区积水问题。倾向与差异方面，多数人认同手机必带，分歧主要在“必要”与“安心”之间——如发言人2认为指甲刀可平替钥匙，而发言人1坚持必须带钥匙；审美上发言人1认为散头发比绑发好看，发言人2假设自己是女生也会选择披发。值得记录的锚点包括：发言人2胡子一天能长几毫米、平均每三天带一次刮胡刀，以及发言人3提到李博家曾被淹。
 # 交流内容
-- **出门必带物品**：发言人1起头问出门必带三样东西，发言人2答`手机`、`充电宝`、`指甲刀`，称指甲刀可磨手掌、戳钥匙；发言人3答`钥匙`，发言人1附和必须带钥匙；发言人4表示必带绑头发的`皮圈`；发言人5称每天带`手机`、`耳机`和`工卡`。
-  - 发言人2已用`电子锁`多年、没有钥匙概念，用指甲刀平替钥匙；还提到以前`扣耳勺`也挂钥匙上。
-  - 发言人4担心钥匙破坏性强，倾向套起来或挂起来；发言人1称自家门是`指纹锁`，出门只需`手机`和`充电线`。
-  - 发言人2上班必带`充电宝`、`手机`、`刮胡刀`三件套，平均`每三天`带一次刮胡刀，因胡子`一天能长几毫米`；发言人5的耳机和工卡直接放单位，靠`刷脸`进门。
-  - 发言人1提到领`夜宵`需带工卡，发言人2称领完即把工卡扔回工位；发言人3补充出门带`纸巾`、下雨带`伞`。
-- **头发打理与个人形象**：发言人2好奇初中男生爱薅女生`头发圈`的原因，发言人1表示无此爱好、认为散头发比绑发好看；发言人2称若自己是女生会披发，因绑发显得`脑袋大`；发言人3建议弄个`公分`两边补点小点。
-  - 发言人2曾想留长发配大胡子，因不好打理放弃；尝试留胡子时被误认为`新疆少数民族`。
-- **下雨天气与居住安全**：发言人1称秋天容易下雨，发言人2好奇为何不是春天；发言人4认为`北京`夏天易下雨，发言人1补充北京下雨少、无季节性。
-  - 发言人3提到每年下雨`园区门口`都是水，`李博`家曾被淹；发言人2建议住`三楼以上`，远离低洼风险。
+- **出门必带物品**：发言人1起头问出门必带三样东西，发言人2答手机、充电宝、指甲刀，并说明指甲刀为多重用途，可刮指甲、磨手掌；发言人3答钥匙，发言人1认同并称自己必须带钥匙。
+  - 发言人2称已用电子锁多年、没有钥匙概念，常用指甲刀平替钥匙，还提到以前会把扣耳勺挂在钥匙上；发言人4指出钥匙破坏性强，会套起来或挂起来。
+  - 发言人4表示一定带绑头发的皮圈，并回应不带皮圈时头发想绑起来不方便；发言人2追问不绑头发是否难受，发言人4确认难受。
+  - 发言人5称每天带手机、耳机和工卡；发言人2回应耳机和工卡直接放单位，靠刷脸进门；发言人1补充领夜宵需工卡，发言人2称领完即放回工位。
+  - 发言人2称上班必带充电宝、手机、刮胡刀，平均每三天带一次，因在家来不及、胡子一天能长几毫米，长了会痒；发言人4问是否胡子长得快，发言人2确认。
+  - 发言人3补充出门带纸巾；发言人1称上班只带手机、不背包不带伞，出差才带手机卡；发言人2建议带砖头重量充电宝可防身。
+- **头发打理与个人形象**：发言人2好奇初中男生爱薅女生头发圈的原因，自称不理解；发言人1表示自己没有此爱好，并认为散头发比绑发好看、不想让女生绑。
+  - 发言人2假设自己是女生会选择披发，因绑发显得脑袋大；发言人3建议弄个公分两边补点小点，发言人2认同。
+  - 发言人2提到高中时梦想留长发和胡子，后因不好打理放弃；曾留大胡子去学校报到，被误认为新疆少数民族，发言人3问是否都尝试过，发言人2确认。
+- **下雨季节与居住安全**：发言人1称秋天容易下雨，发言人2好奇为何不是春天，发言人4认为北京夏天易下雨，发言人1补充夏天易下暴雨。
+  - 发言人3提到每年下雨园区门口都是水，李博家曾被淹；发言人2问是否住一楼，发言人3称与其地势有关，发言人2建议住三楼以上。
 # 关键原话
-&gt; 手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。
-- 发言人2回答发言人1提出的“出门必带三样东西”问题，解释指甲刀的多重用途。
-&gt; 对呀，我必须带钥匙，不带钥匙就行。
-- 发言人1回应发言人3提到的“钥匙”，强调自己出门必带钥匙。
-&gt; 我我已经好多年的电子锁了，我都没什么钥匙的概念了都。然后所以说拿指甲刀来平替钥匙了。
-- 发言人2说明自己因长期使用电子锁而用指甲刀替代钥匙。
-&gt; 我一定会带一个那个皮圈就绑头发的。
-- 发言人4在讨论出门必带物品时提到必带绑头发的皮圈。
-&gt; 对，所以说我上班必带三件套，充电宝、手机、刮胡刀。
-- 发言人2总结自己上班必带物品，此前提到胡子一天能长几毫米、平均每三天带一次刮胡刀。
-&gt; 我现在每天就是手机、耳机和工卡。
-- 发言人5回应“没人上班带耳机吗”，说明自己每天必带物品。
-&gt; 我觉得北京是夏天能易下雨的。
-- 发言人4回应发言人2关于“秋天容易下雨”的疑问，提出北京夏天易下雨。
-&gt; 是我记得每年的下雨，嗯，都都那个园区门口都是水。李博还之前不是还就是开幕的那个地方还被淹了吗？
-- 发言人3在讨论下雨天气时提到园区门口积水及李博家曾被淹。
+&gt; “手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。”
+- 背景：发言人1问出门必带三样东西，发言人2作答并解释指甲刀用途。
+&gt; “我家的家钥匙。”
+- 背景：发言人4回应出门必带物品话题，提到家钥匙。
+&gt; “我我已经好多年的电子锁了，我都没什么钥匙的概念了都。然后所以说拿指甲刀来平替钥匙了。”
+- 背景：发言人2回应钥匙话题，说明自己用电子锁多年、以指甲刀替代钥匙。
+&gt; “我一定会带一个那个皮圈就绑头发的。”
+- 背景：发言人4在出门必带物品讨论中补充自己必带绑头发皮圈。
+&gt; “对，所以说我上班必带三件套，充电宝、手机、刮胡刀。”
+- 背景：发言人2回应上班必带物品话题，列出自己的三件套。
+&gt; “我现在每天就是手机、耳机和工卡。”
+- 背景：发言人5回应上班必带物品话题，列出自己的每日携带物。
+&gt; “因为初中那会好多男生去薅女生的头发，我不知道他们为什么那喜欢这样，然后我也不太理解这个兴趣点在哪里。”
+- 背景：发言人2在头发打理话题中表达对初中男生薅女生头发圈行为的不解。
+&gt; “反正那要这样的话，我觉得还是得远离，三楼以下还是得三楼以上？那么住着，对不对？”
+- 背景：发言人2回应李博家被淹一事，建议居住选三楼以上。
 # 共识与分歧
-- **共识**：**出门必带物品以实用与个人习惯为核心**，多数人认同手机、钥匙、充电宝等属于高频刚需，理由集中在“不带会带来实际不便”（如发言人1强调“不带钥匙不行”、发言人2因胡子长得快而必带刮胡刀），分歧主要落在“必要”与“安心”之间——如发言人2用指甲刀平替钥匙、将充电宝视为“既能充电也能防身”的物件，属于习惯性安心；而发言人5带耳机、工卡则更贴近工作场景的必要性。
-- **分歧**：在头发打理上呈现审美差异——发言人1认为散头发比绑发好看，发言人2从自身角度认为绑发显脑袋大、倾向披发，发言人4则因实际需要（绑头发）必带皮圈；在天气判断上存在经验差异——发言人4认为北京夏天易下雨，发言人1认为北京下雨少且无季节性，发言人3以园区门口积水、李博家被淹为例佐证夏季暴雨风险，发言人2据此提出“住三楼以上”的居住安全建议。
-- **倾向**：本场为分享漫谈型，未形成明确结论，整体倾向是**出门物品因人而异，以个人习惯和实际场景为转移**；对居住安全的讨论虽由天气引出，但发言人均以自身经验或听闻为依据，未上升到统一行动建议。
+- **共识**：**手机是出门必带的核心物品**，多数人默认手机不可或缺，且电子锁普及后钥匙的必要性下降，发言人均认同这一趋势。
+- **分歧一（必要 vs 安心）**：钥匙是否必带存在分歧。发言人1坚持必须带钥匙，而发言人2因多年使用电子锁已无钥匙概念，用指甲刀平替；分歧性质属于*习惯差异与安全感需求不同*，而非功能必要性的实质对立。
+- **分歧二（审美差异）**：头发绑与不绑的偏好不同。发言人1认为散头发更好看，发言人2假设自己是女生也会选择披发以显脸小，发言人3则建议弄个公分两边补点小点；分歧性质为*个人审美差异*，无对错之分。
+- **本场倾向**：以分享个人习惯为主，未形成明确结论。多数人认同出门带物以实用和便捷为导向，如发言人2强调刮胡刀因胡子长得快（一天几毫米）而成为上班必带，发言人5则倾向手机、耳机、工卡三件套；分歧仅在*具体物品的取舍依据*，即功能必需与个人舒适感之间的权重不同。
 # 延伸话题与后续
-- **秋天容易下雨还是春天容易下雨**：发言人1提到秋天容易下雨，发言人2好奇为何不是春天，发言人4认为北京夏天容易下雨，发言人1补充北京下雨少且无季节性，讨论未形成定论。
-- **李博家被淹的后续**：发言人3提到每年下雨园区门口积水，李博家曾被淹，发言人2建议住三楼以上，未再深入。</t>
+- **初中男生薅女生头发圈的原因**：发言人2提出好奇初中时期很多男生喜欢薅女生头发圈的兴趣点在哪里，发言人1表示自己没有特别爱好、不想薅，讨论未深入即转向其他话题。
+- **秋天与春天哪个季节更容易下雨**：发言人1提到秋天容易下雨，发言人2好奇为何不是通常认为的春天，发言人4认为北京夏天容易下雨，发言人3未听清问题，讨论未形成定论即被叫停。</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>30.4</v>
+        <v>31.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3851/2252</t>
+          <t>3851/2307</t>
         </is>
       </c>
     </row>
@@ -15949,46 +15991,50 @@
       <c r="C46" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议为开放式漫谈，由发言人1发起，围绕“手机里最常用的三个APP”展开，共5位成员（发言人1至发言人5）参与，无正式议程。讨论由常用APP话题自然延伸至AI助手、视频播放器、音乐平台及歌手偏好等议题，具体包括：常用APP与AI助手使用习惯、视频与播放器APP使用情况、音乐APP与音乐偏好。整体以分享个人使用经验与观点为主，未形成统一结论。讨论按话题逐块推进，从APP清单切入，经AI助手准确性争议、视频平台版权与广告问题，过渡至音乐平台选择与听歌场景，最后以对Taylor Swift等歌手的偏好交流收尾。会议提及“单框架手机”“卓翼通”“虾扎”等专名，以及“柏林地铁”等场景锚点。
+本次会议为多人参与的日常交流，由发言人1发起，围绕手机常用APP、AI助手、视频平台、音乐APP及歌手喜好等话题展开，与会者分别分享个人使用习惯与偏好。讨论由发言人1以「手机里最常用的三个APP」提问开场，随后依次谈及AI助手使用与信任度、视频平台与播放器偏好、音乐APP与听歌场景、歌手与乐队喜好，整体按话题逐块推进，属漫谈分享型交流，以分享观点为主，未形成统一结论。与会者共5人，按原文编号为发言人1至发言人5。讨论中涉及的具体专名包括知乎、小红书、谷歌、微信、抖音、淘宝、京东、小布小布、豆包、B站、YouTube、腾讯视频、爱奇艺、优酷、芒果TV、网易云、酷狗、酷我、虾扎、Taylor Swift、五月天、谢霆锋等。
 # 发言要点
-## 常用APP与AI助手使用习惯
-- **发言人2**：最常用APP为知乎、小红书、谷歌；不常用AI软件，因不确定其回答是否正确，仍停留在浏览器、纸质地图、尺子、圆规和铅笔标注的思维模式。
-- **发言人3**：最常用微信、抖音、淘宝、京东等；已下载豆包AI助手，认为AI小助手回答更精准、总结性更强。
-- **发言人4**：最常用微信、小红书；手机用小布小布AI助手，已不用浏览器直接搜索。
-- **发言人5**：已下载豆包AI助手。
-- **发言人1**：使用百度千问等AI助手；对AI回答准确性提出质疑「你能判断他说的是对的吗」。
-## 视频与播放器APP使用情况
-- **发言人5**：常用B站和YouTube，希望中英混杂内容能被识别；指出单框架手机现在连YouTube都下不了。
+## 手机常用APP与AI助手使用习惯
+- **发言人2**：最常用APP为知乎、小红书、谷歌；表示不确定AI回答是否正确，仍停留在浏览器、纸质地图、尺子圆规铅笔标注的思维模式，自比「大家在用GPS，我还在用纸质地图」。
+- **发言人3**：最常用微信、抖音、淘宝、京东；认为AI小助手比浏览器更全面、回答更精准、总结性更强，自己也下载了豆包。
+- **发言人4**：最常用微信、小红书，另用手机自带的小布小布，称「现在都不用浏览器了，直接搜小布小布」。
+- **发言人5**：最常用微信；指出小布小布即豆包。
+- **发言人1**：手机装有百度千问、吉米等多个AI应用，未装元宝；反问「你能判断他说的是对的吗」，对AI回答准确性提出质疑。
+## 视频平台与播放器偏好
+- **发言人5**：B站用得较多，也看YouTube，希望中英混杂内容能被识别；指出单框架手机现在连YouTube都下不了了。
 - **发言人4**：指出YouTube手机一般翻不了墙。
-- **发言人1**：发现国内付费电视剧在YouTube上免费。
-- **发言人2**：YouTube上部分内容仍需付费，但一些小网站可免费观看，因大平台有版权纠纷需付费；广告时间太长，倾向直接用B站观看。
-- **发言人3**：常用腾讯视频、爱奇艺、优酷、芒果TV等播放器；提到可通过看广告获得VIP时长。
-- **发言人5**：APP太多，不知道开哪个VIP。
-## 音乐APP与音乐偏好
-- **发言人5**：常用网易云音乐；单框架手机网易云不适配，现用卓翼通。
-- **发言人2**：以前常用酷狗、酷我；提到欧美音乐平台虾扎有更多欧美演唱会版本，但大牌音乐因版权纠纷播不出来；在柏林坐地铁时听音乐代入感强，因地铁较安静。
-- **发言人1**：认为虾扎平台唱的多是小众歌手；上班时听音乐。
-- **发言人4**：通勤路上听音乐，需用降噪耳机。
-- **发言人3**：最近喜欢谢霆锋，因其演唱会感染力强、氛围好；提到可通过看广告获得VIP时长。
-- **发言人2**：疑惑Taylor Swift为何重新火起来——2010年代开头已火，后因绯闻消沉，但对九零后和零零后影响都很深；提到其与猫头鹰之城主唱亚当杨的绯闻，称当时东南卫视台湾节目讲过。
+- **发言人1**：发现国内付费电视剧在YouTube上不要钱。
+- **发言人2**：认为大平台因版权纠纷需付费，小网站没有版权纠纷所以免费；自己反而找到一些小网站不用花钱。
+- **发言人3**：常用腾讯视频、爱奇艺、优酷、芒果TV等播放器，会点进去看有没有想看的。
+- **发言人2**：抱怨广告时间太长「耗不起了」，选择用B站直接看，不愿等广告；对开VIP表示犹豫。
+- **发言人5**：认为APP太多，不知道开哪个VIP。
+## 音乐APP与听歌习惯
+- **发言人5**：网易云用得较多；指出单框架手机网易云一直不适配，现在全靠卓翼通，其他APP基本都适配了。
+- **发言人2**：以前常用酷狗、酷我；提及美国音乐平台虾扎，认为其欧美演唱会版本比国内网易云更多，但小众翻唱多，大版权歌曲因纠纷播不出来。
+- **发言人1**：上班时候听音乐；认为虾扎唱的多是小众歌手。
+- **发言人4**：通勤路上听音乐，需配降噪耳机。
+- **发言人2**：认为在柏林坐地铁时听音乐代入感强，因地铁比较安静，可以听音乐看景。
+## 歌手与乐队喜好
+- **发言人3**：最近刷到谢霆锋演Taylor Swift，开始喜欢谢霆锋，提及《玉蝴蝶》等老歌，记不清年份。
+- **发言人2**：疑惑Taylor Swift为何重新火起来——中学时（2010年代开头）她已很火，后因绯闻消沉很长一段时间，现在对九零后和零零后影响都很深；提及《Speak Now》《Back To December》《Love Story》等歌，并回忆她与猫头鹰之城主唱亚当杨的绯闻，称是当年从东南卫视台湾节目看到的。
+- **发言人1**：认为五月天以前挺好，但新发的作品「唱不上去了」。
+- **发言人4**：对Taylor Swift绯闻「没有很关注」，但承认她确有全球影响力。
 # 共识形成
-- **一致意见**：与会者普遍认可AI助手比浏览器更全面、回答更精准、总结性更强（发言人3），但发言人2明确表示不常用AI软件，因不确定其回答是否正确，仍停留在浏览器、纸质地图、尺子、圆规和铅笔标注的思维模式，形成**AI助手便捷性与准确性信任度**的倾向性分歧。
-- **视频平台分歧**：发言人1发现国内付费电视剧在YouTube上免费，发言人2指出YouTube上部分内容仍需付费，但一些小网站可免费观看，因大平台有版权纠纷；发言人2抱怨播放器广告时间太长，倾向直接用B站观看，发言人3提出可通过看广告获得VIP时长。
-- **音乐平台分歧**：发言人2提到欧美音乐平台虾扎有更多欧美演唱会版本，发言人1认为其多为小众歌手，发言人2指出因版权纠纷大牌音乐播不出来；发言人5因单框架手机网易云不适配，现用卓翼通。
-- **歌手偏好**：发言人3最近喜欢谢霆锋，发言人2疑惑Taylor Swift为何重新火起来，称其2010年代已火，后因绯闻消沉，未得到明确解答。
+- **一致意见**：与会者普遍认可AI助手在回答全面性、精准度与总结性上优于传统浏览器搜索，发言人3明确表示「AI这个小助手更全面一点，回答的更精准一点，然后总结性比较强」；发言人2虽持保留态度，但承认自己「比大家落后了一代」，仍停留在浏览器、纸质地图、尺子铅笔标注的思维模式。
+- **主要分歧**：围绕AI回答可信度，发言人1提出「你能判断他说的是对的吗」的质疑，发言人2回应称不确定AI回答是否正确，因此不愿使用AI软件；发言人3则以自身使用体验表示认可，双方未就此达成一致。
+- **倾向性认识**：在视频平台方面，发言人2提出大平台因版权纠纷需付费、小网站无版权纠纷可免费观看的解释，发言人5补充小网站「一般会有那种广告感觉」，与会者未再提出异议；在音乐平台方面，发言人2认为美国平台虾扎的欧美演唱会版本更多，但小众翻唱多、大版权歌曲因纠纷播不出来，发言人1补充其「唱的都是一些小众歌手」，双方观点相互印证。
 # 待探讨问题与后续
-- **未定论**：发言人2疑惑Taylor Swift为何在近期重新火起来，称其2010年代已火、后因绯闻消沉，但未得到明确解答。
-- **未确认**：发言人2提及Taylor Swift与猫头鹰之城主唱亚当·杨曾传出绯闻，并称其当时曾向对方表白，发言人4表示未关注此事，该说法未获其他成员证实。
-- **未确认**：发言人2提到欧美音乐平台「虾扎」有更多欧美演唱会版本，但发言人1认为其多为小众歌手，发言人2指出因版权纠纷大牌音乐播不出来，该平台的具体情况未进一步核实。
-- **待核实**：发言人5指出单框架手机网易云音乐不适配、需用「卓翼通」替代，其他成员未回应，该问题是否普遍存在未获讨论。</t>
+- **未确认**：发言人2对Taylor Swift（梅梅）在2010年代初期走红、后因绯闻消沉、近期重新火起来的原因表示疑惑，询问在场者看法，发言人4回应「没有很关注」，未获进一步解答。
+- **未确认**：发言人2提及美国音乐平台「虾扎」时，发言人4未听懂并追问「你说英文吧」，发言人2解释其为美国音乐平台后，未再深入讨论该平台的具体情况。
+- **未确认**：发言人2询问大家对五月天、周杰伦作品的看法，发言人1回应「五月天以前还挺好的，但新发的作品唱不上去了」，未展开具体评价。
+- **未确认**：发言人2提到Taylor Swift与猫头鹰之城（Owl City）主唱亚当·杨的绯闻及表白传闻，询问在场者是否了解，发言人4回应「没有很关注」，话题未继续。</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>36.7</v>
+        <v>40.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4259/1974</t>
+          <t>4259/2313</t>
         </is>
       </c>
     </row>
@@ -16165,59 +16211,61 @@
       <c r="C47" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论由主持人（发言人1）发起，围绕2022年俄乌战争以来俄军的战场表现展开，对比游戏与影视中的俄军形象，并延伸至俄罗斯的地缘政治认知、旅游与文化印象。讨论面向对军事、地缘政治及俄罗斯文化感兴趣的参与者，以开放座谈形式进行。板块涵盖俄军在俄乌战争中的实际表现、游戏与影视中的俄军形象、俄罗斯的地缘政治与欧洲认知、俄罗斯旅游与文化印象。核心判断包括：俄军单兵素质强但后勤与指挥拉垮，形容为“矮脚巨人”；俄军从闪电战转为持久战，双方重装备耗尽，陷入战壕对峙与无人机互炸状态；欧洲将乌克兰视为“欧洲之门”，将俄罗斯视为亚洲游牧民族，因此支持乌克兰以阻挡俄罗斯。锚点案例包括《战地风云》《使命召唤》《红警》等游戏中的俄军形象、圣彼得堡东宫（世界四大艺术博物馆之一）、俄罗斯以探险队名义掠夺多国藏品。对听众而言，有助于理解俄军表现背后的多重因素及俄罗斯与欧洲的地缘认知差异。
+本次讨论由主持人（发言人1）发起，围绕2022年俄乌战争以来俄军在战场上的表现展开，旨在探讨俄军表现是否为其真实状态，并交流对俄军及俄罗斯的整体印象。讨论覆盖四个板块：俄军在俄乌战争中的表现、游戏中的俄军形象与现实对比、欧洲对俄罗斯的认知、俄罗斯旅游与文化。核心判断包括：俄军单兵素质强但后勤和指挥拉垮，被形容为“矮脚巨人”；战争已从“钢铁洪流”变成“菜鸡互啄”的持久消耗战；欧洲将乌克兰视为“欧洲之门”，必须守住以将俄罗斯挡在亚洲之外。讨论以《战地风云》《使命召唤》《红警》等游戏中的俄军形象为锚点，并提及2014年克里米亚事件、普京信息茧房、情报经费贪污等案例。对听众而言，本讨论有助于理解俄乌冲突的深层背景及西方视角下的俄罗斯形象。
 # 核心观点与论证
-## 俄军表现与预期严重不符
-- **战争预期落空**：2022年俄乌战争爆发时，全世界认为战争天平会向俄罗斯一边倒，基辅会很快被占领、乌克兰会被消灭、泽连斯基会流亡；实际泽连斯基扛住进攻，俄军被从基辅打回白俄罗斯和乌克兰边境。
-- **从闪电战变持久战**：俄军基层官兵收到命令时以为是去演习，结果演着演着进入乌克兰；第一批部队遭遇的是民兵自发抵抗而非军队有组织进攻，一来二去从闪电战变成持久战。
-- **战场形态退化**：双方重装备耗光后，只能隔着战壕互相扔手雷或用无人机互炸，发言人1形容为「从钢铁洪流变成了菜鸡互啄」；发言人4认为俄乌战场与二战相比没多大进步，只是多了无人机。
-- **单兵强而体系弱**：发言人1总结俄军「单兵素质很厉害，但总体很拉垮，主要后勤和指挥上」，形容为「矮脚巨人」——像柯基一样腿短撑不起庞大身躯。
-## 俄军表现不佳的原因分析
-- **普京信息茧房**：发言人1认为普京「活在他自己的信息茧房里」，对战场真实情况缺乏准确判断。
-- **情报经费被贪污**：用于策反乌克兰官员的经费被情报官员贪污瓜分，普京真要进攻时乌克兰高官根本没收到策反经费。
-- **乌克兰民族仇恨**：2014年俄罗斯占领克里米亚后，乌克兰上下迸发民族仇恨，发言人1类比为「九一八事变」式耻辱——一枪不发丢掉整个克里米亚，民众对政府无能与腐败非常不满。
-- **装备依赖伊朗**：发言人1指出俄罗斯的无人机靠伊朗提供，乌克兰则靠北约持续输血，形成类似越战的消耗战格局。
-## 游戏与影视中的俄军形象
-- **游戏形象与现实反差**：发言人1提及《战地风云》《使命召唤》《红警》等游戏中的俄军或苏联红军形象，与现实中俄军表现有「360度的改观」。
-- **西方游戏刻意抹黑**：发言人2认为《红警》是美国为黑苏联而制作；发言人4补充称西方主导的游戏几乎都把苏联描绘成反面角色——很猛、很变态、研究邪乎武器、规模夸张。
-- **意识形态丑化**：发言人1指出西方把共产主义解放世界的思想抹黑成`心灵控制器`（《红警》中的武器），把毛子形容成暴力美学的形象代言。
-## 欧洲地缘认知与乌克兰地位
-- **欧洲之门**：乌克兰在欧洲人认知中被称为`欧洲之门`；欧洲人认为欧亚分界线在乌克兰而非乌拉尔山脉——白俄罗斯大部分是沼泽地，无法形成大规模运输通道走廊。
-- **俄罗斯被当亚洲人**：欧洲人把俄罗斯人当亚洲野蛮人看待，类似《冰封王座》中贝加尔湖一带半兽人的反派角色；俄罗斯被蒙古人统治二百年，不被欧洲认可接纳，被视为「长着欧洲面孔的亚洲游牧民族」。
-- **欧洲支援乌克兰的动机**：欧洲必须武装并守好乌克兰，把俄罗斯挡在亚洲之外；若俄罗斯握紧乌克兰，欧洲会「再一次生活在曾经的阴影之下」——唇亡齿寒的道理欧洲人明白。
-- **美国与欧洲态度差异**：发言人1称在美国人认知中俄罗斯「既不是朋友也不是敌人，就是一个普通国家」；但在波兰、乌克兰、波罗的海三国等东欧国家眼中，俄罗斯就是敌人、蛮子、半兽人。
+## 俄军单兵强而体系弱
+- **单兵素质与体系反差**：发言人1总结俄军“单兵素质很厉害，但总体很拉垮，主要后勤和指挥上”，以“矮脚巨人”作比，称其像柯基“腿特别短，支撑不起庞大的身子”。
+- **战场形态退化**：发言人1指出双方重装备耗光后，只能“隔着战壕互相扔手雷，或者互相用无人机互炸”，战争从“钢铁洪流”变成“菜鸡互啄”的持久消耗战。
+- **与二战对比**：发言人4认为俄乌战场“跟二战时候也没啥进步，多了点无人机”，仍以扔手雷等近战方式为主，技术含量有限。
+- **防守反击特点**：发言人4提出俄军“主动进攻感觉一坨”，但被打到“家破国亡”时能迸发战斗力、擅长“打防反”，主动进攻表现差。
+## 普京信息茧房与战前误判
+- **情报经费被贪污**：发言人1称普京“活在他自己的信息茧房里”，其下属情报官员将用于策反乌克兰官员的经费全部贪污瓜分，普京未料真要进攻乌克兰，结果乌克兰高官未收到策反经费。
+- **基层官兵不知情**：发言人1指出俄军基层官兵2022年收到命令时“还以为是去演习的”，结果“演着演着就进乌克兰”，第一批部队遭遇的是民兵自发抵抗而非军队有组织进攻。
+- **克里米亚埋下仇恨**：发言人1称2014年俄罗斯占领克里米亚后，乌克兰上下迸发民族仇恨，类似“九一八事变”的耻辱感——“一枪不发，丢掉整个克里米亚”，民众对当权者无能与腐败非常不满。
+- **闪电战变持久战**：发言人1表示因上述误判与抵抗，“一来二去，从闪电战变成了持久战”，与游戏中的俄军形象形成“360度”反差。
+## 游戏中的俄军形象被西方塑造
+- **西方游戏主导叙事**：发言人2认为红警“是美国做出来为了黑苏联的”，发言人4补充称西方主导的游戏里苏联形象“都是反面的、很猛、很变态”，研究“非常邪乎的武器”，规模夸张。
+- **心灵控制器隐喻**：发言人1举例红警中的“心灵控制器”，认为西方把共产主义“解放世界的思想”抹黑成心灵控制，把苏联形容成“暴力美学的形象代言”。
+- **游戏与现实反差**：发言人1列举《战地风云》《战地三》《使命召唤》《红警》等游戏，称其中俄军或苏联红军形象与现实“最起码有360度的改过”。
+## 欧洲将俄罗斯视为亚洲蛮族
+- **欧亚分界线认知差异**：发言人1称欧洲人认为欧亚分界线在乌克兰，因白俄罗斯大部分是沼泽地、缺乏大规模运输通道走廊，故欧洲始终把俄罗斯当亚洲人看待。
+- **蒙古统治历史影响**：发言人1指出俄罗斯被蒙古人统治二百年，不被欧洲人认可接纳，被视为“长着欧洲面孔的亚洲游牧民族”，类似《冰封王座》中“半兽人”的反派角色。
+- **乌克兰是欧洲之门**：发言人1称乌克兰在欧洲认知中被称为“欧洲之门”，欧洲必须“武装并守好乌克兰，把俄罗斯挡在亚洲之外”，否则欧洲会“再一次生活在曾经的阴影之下”。
+- **唇亡齿寒的支援逻辑**：发言人1认为欧洲自发支援乌克兰、不让俄罗斯打赢，是因为“唇亡齿寒”——若俄罗斯握紧乌克兰，欧洲将面临威胁，这也是乌克兰“死活不能向俄罗斯妥协的根本原因”。
+## 俄乌战争的地缘与历史逻辑
+- **乌克兰是俄罗斯立国资本**：发言人1指出乌克兰军队前身是苏联红军重要组成部分，俄罗斯立国也靠乌克兰作为立国资本，因此俄罗斯“一定要把乌克兰握在自己手里”。
+- **失去乌克兰沦为边缘国家**：发言人1称没有乌克兰的俄罗斯帝国“终究只是沦为边缘亚洲国家”，不会被欧洲待见，这是俄罗斯执意控制乌克兰的深层动因。
+- **越战式消耗战**：发言人1将俄乌战争类比越战——乌克兰由北约“持续不断输血”，俄罗斯靠伊朗提供无人机，双方形成长期消耗态势。
 ## 俄罗斯旅游与文化印象
-- **东宫值得一去**：发言人1推荐圣彼得堡东宫，称其为`世界四大艺术博物馆之一`，连续三次参观不同区域都没看完馆藏珍宝，圣彼得堡夏天不错。
-- **藏品来源多元**：俄罗斯以探险队名义从全球掠夺藏品——西至德国、法国、荷兰（含二战打进德国运回纳粹产品及王室联姻赠品），东至朝鲜半岛、蒙古、西藏、西夏王陵、敦煌，南至阿富汗、中亚、埃及、北非、奥斯曼帝国土耳其。
-- **签证与入境经历**：发言人2提到去俄罗斯旅游后办美签可能被拒；发言人1分享因多次去俄罗斯，在美国边境入口被拦下盘问去俄目的，差点被怀疑是间谍。
+- **东宫值得一去**：发言人1推荐圣彼得堡的东宫，称其为“世界四大艺术博物馆之一”，自己连续去三次、不同区域都没逛完，夏天去圣彼得堡“还是不错的”。
+- **藏品来源多元**：发言人1介绍东宫藏品来源包括列强殖民掠夺、探险队名义获取、二战打进德国后运回纳粹藏品、王室联姻赠送品，地域覆盖欧洲（德国、法国、荷兰）、东亚（朝鲜半岛、蒙古、西藏、西夏王陵、敦煌）、南向（阿富汗、中亚、埃及、北非、奥斯曼土耳其）等地。
+- **俄罗斯族为主体**：发言人1称俄罗斯虽境内有多个共和国，但“总的来说还是以俄罗斯族为主”，其东扩过程类似美国西进运动，源源不断淘金移民。
 # 金句总结
-&gt; 俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上。
-- 讲到俄军在俄乌战争中的整体表现，针对其单兵能力与后勤指挥体系的落差。
-&gt; 从一种钢铁洪流变成了最后的菜鸡互啄。
-- 讲到双方重装备耗尽后，战场陷入战壕对峙与无人机互炸的状态。
-&gt; 没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。
-- 讲到俄罗斯必须将乌克兰握在手中的地缘政治原因。
-&gt; 欧洲的边界是在乌克兰，一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。
-- 讲到欧洲支援乌克兰以阻挡俄罗斯、避免欧洲再次生活在阴影下的战略考量。
-&gt; 长着欧洲面孔的亚洲游牧民族。
-- 讲到欧洲人因俄罗斯被蒙古统治二百年而不予认可，将其视为亚洲人的认知。
+&gt; “俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上。”
+- 背景：总结俄军在俄乌战争中的整体表现，指出其单兵能力与后勤指挥体系之间的落差。
+&gt; “从一种钢铁洪流变成了最后的菜鸡互啄。”
+- 背景：描述双方重装备耗光后，战场形态从大规模装甲突击退化为战壕互扔手雷与无人机互炸的消耗战。
+&gt; “只能说是普京飘了，他活在他自己的一个信息茧房里边。”
+- 背景：分析俄军初期进攻失利的原因，认为普京基于被贪污经费所扭曲的情报做出了误判。
+&gt; “乌克兰上下迸发出了一种民族间的一种仇恨，就会在我们看来就有一种类似于像九一八事变的一种耻辱。”
+- 背景：解释2014年克里米亚被占后乌克兰民间的抵抗情绪，以此说明乌军顽强抵抗的社会根源。
+&gt; “没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。”
+- 背景：论证俄罗斯必须将乌克兰握在手中的地缘政治逻辑，认为失去乌克兰将使俄罗斯被欧洲边缘化。
+&gt; “欧洲的边界是在乌克兰，所以说一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。”
+- 背景：阐述欧洲支援乌克兰的根本动机，即视乌克兰为“欧洲之门”，必须以此阻挡俄罗斯进入欧洲。
+&gt; “俄罗斯被蒙古人统治过二百年，所以说就是他们不被欧洲人所认可、接纳，终究就是被当成是亚洲游牧民族来看待。”
+- 背景：解释欧洲将俄罗斯视为“半兽人”式他者的历史根源，即蒙古统治经历使其不被视为欧洲文明一员。
 # Q&amp;A 环节
-**发言人4**：俄罗斯打仗是不是得给它打到要家破国亡了，才能迸发出战斗力打防守反击？主动进攻感觉就不行。
-**发言人1**：可以这么说。俄军单兵素质很厉害，但总体拉垮，主要在后勤和指挥上，像“矮脚巨人”，腿特别短，支撑不起庞大的身子。2022年开战时普京活在自己的信息茧房里，底下情报官员把策反乌克兰官员的经费全贪污瓜分了，没想到普京真会进攻；基层官兵也以为是去演习，结果演着演着就进了乌克兰，第一批部队遭遇的是民兵自发抵抗，不是军队有组织进攻，一来二去从闪电战变成了持久战。
-**发言人4**：感觉俄乌战场打得跟二战时候也没啥进步，多了点无人机，还是扔手雷，不太先进。
-**发言人1**：双方重装备都耗光了，只能隔着战壕互相扔手雷、用无人机互炸，从钢铁洪流变成了菜鸡互啄。俄罗斯的无人机靠伊朗给，乌克兰靠北约持续输血，有点像越战的形式——乌克兰相当于北约，俄罗斯相当于越战时的美国，就这么耗着。
-**发言人2**：去俄罗斯旅游之后，签证上会留记录，办美签的时候会被拒吧？
-**发言人1**：对，我上次去美国，因为去过好几次俄罗斯，在边境入口就被拦下来盘问去俄罗斯干嘛，差点被怀疑是间谍。美国人对咱们既不当朋友也不当敌人，但东欧国家——波兰、乌克兰、波罗的海三国——是把俄罗斯当敌人、当蛮子看的。不过圣彼得堡的东宫还是值得去，世界四大艺术博物馆之一，我连续去了三次，不同区域都没逛完。
-**发言人4**：俄罗斯地域那么宽阔，远东地区和欧洲那头差别大不大？
-**发言人1**：总的来说还是以俄罗斯族为主，他们俄国东扩也像美国西进似的，源源不断淘金移民。俄罗斯历史上以探险队名义从欧洲、中东、东亚掠夺了不少藏品，东宫里能看到德国、法国、荷兰的，也有朝鲜半岛、蒙古、西藏、西夏王陵、敦煌的，还有阿富汗、中亚、埃及、北非、奥斯曼土耳其时期的藏品。</t>
+**发言人4**：俄罗斯是不是欧洲那边跟亚洲这边差别很大？地域那么宽阔，远东地区的风格和欧洲那头应该不一样吧？
+**发言人1**：总的来说还是以俄罗斯族为主，毕竟他们又是俄国东扩，也像美国西进似的，源源不断地淘金移民，就这样的。</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>45.2</v>
+        <v>50.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6103/3045</t>
+          <t>6103/2892</t>
         </is>
       </c>
     </row>
@@ -16320,51 +16368,52 @@
       <c r="C48" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论由主持人发言人1组织，围绕电影《南京照相馆》展开，与会者分享了观影印象，并延伸至南京大屠杀的历史背景、真实与虚构细节及各地抗战纪念馆的参观体验。发言人1指出，电影主要人物为虚构，但照片拍摄真实，实际由两名美国传教士拍摄日军暴行，中国照片冲洗员偷偷拷贝后于战后交给国民政府军事法庭作为审判证据；中华门城墙战斗、挹江门撤退惨案及战后审判谷寿夫等主犯均为真实历史。发言人1还分析了南京大屠杀的成因，提及日军自九一八事变以来首次遭遇淞沪会战的迎头痛击、日本屠城传统及高压武士道精神，并指出松井石根曾下令避免烧杀抢掠，因生病被替换后，朝香宫鸠彦亲王发布“不留俘虏”命令导致军纪失控。与会者还分享了沈阳伪满洲国博物馆、唐山大地震纪念馆、上海淞沪会战纪念馆等地的参观经历，并提及南京大屠杀纪念馆预约困难。本次讨论面向对历史题材电影及抗战历史感兴趣的听众，有助于厘清电影叙事与史实的边界，深化对南京大屠杀历史成因与记忆传承的认识。
+本次会议围绕电影《南京照相馆》展开观影印象分享与历史背景交流，由发言人1主持并担任主要讲解者，与会者包括发言人2、3、4、5。会议旨在通过电影这一载体，增进对南京大屠杀历史背景、真实与虚构细节的认知，并延伸至各地抗战纪念馆参观体验的讨论。讨论覆盖了观影印象、历史背景介绍、真实与虚构细节辨析、抗战纪念馆参观体验、南京大屠杀历史原因分析以及日本对南京大屠杀的承认问题等板块。核心判断包括：电影主要人物为虚构，但照片拍摄真实，实际由两名美国传教士拍摄日军暴行，中国照片冲洗人员偷偷拷贝后于战后提交国民政府军事法庭作为审判证据；日军自九一八事变以来首次遭遇迎头痛击，因缺乏军纪约束及长期战争导致人性泯灭，最终引发南京大屠杀。关键锚点包括1937年8月13日淞沪抗战、松井石根被替换后朝香宫鸠彦亲王发布不留俘虏命令、中华门城墙战斗及挹江门撤退惨案等真实历史细节。对听众而言，本次讨论有助于区分电影艺术加工与历史事实，深化对南京大屠杀历史成因及国人历史关注度的理解。
 # 核心观点与论证
-## 电影主要人物虚构，照片拍摄真实
-- **人物虚构**：电影中主角与日本军官建立友谊的情节为虚构，发言人1确认主要人物并非真实历史人物。
-- **照片真实**：照片拍摄本身真实，但方式与电影描述不同——实际由两名美国传教士拍摄日军暴行。
-- **照片来源**：当时一名负责为日本人冲洗照片的中国冲洗员无意间发现日军暴行照片，因属日本禁文而偷偷拷贝藏起。
-- **照片用途**：抗战结束后，该冲洗员将照片递交给国民政府军事法庭，作为审判日本战犯的证据。
-## 南京大屠杀历史背景与成因
-- **战争进程**：1937年8月13日国民党军队在上海与日军激战，后因实力原因撤退，日军从上海一路追击至南京。
-- **抵抗空白**：自1931年九一八事变至八一三淞沪抗战前，日军占领东北、华北均未遭遇成规模抵抗，淞沪抗战是日军首次迎头痛击。
-- **军纪失控**：日军因战场伤亡惨重、长达四个月作战已杀红眼，攻破南京后缺乏法律与军纪约束，导致南京大屠杀发生。
-- **日军心态**：发言人1分析日军遭受前所未有的侮辱感与战场应激创伤，结合日本攻破城镇后屠城的传统，以及高压武士道精神下的欺凌与霸凌背景，日军以放纵作为宣泄。
-## 松井石根与朝香宫鸠彦的指挥更替
-- **松井石根命令**：原日军指挥官松井石根因生病被临时替换，他曾接连发布命令，要求避免日军在上海至南京沿线烧杀抢掠，以免招致中国军民反感、增强抵抗意志。
-- **朝香宫鸠彦接任**：接任者为裕仁亲王的叔叔朝香宫鸠彦亲王，他是日本国内脱亚入欧思想的狂热追随者，认为亚洲国家除日本外皆低贱。
-- **不留俘虏命令**：朝香宫鸠彦上任后发布第一道命令为「不留俘虏」，日军第一时间格杀勿论，随后蔓延至对老百姓群体，最终导致南京大屠杀与日军军纪失控。
-## 电影中的真实历史细节
-- **中华门战斗**：电影开头中华门城墙的战斗是真实历史细节，反映日军进攻南京所遭受的抵抗。
-- **挹江门惨案**：电影中挹江门撤退场景真实——宪兵未让军民撤出，守挹江门部队未收到撤退命令，双方信息差导致惨案发生。
-- **战后审判**：电影尾声审判为真实历史——打进南京的谷寿夫（第六师团师团长）及多名南京大屠杀主犯（基层日军军官）当时被枪决。
-- **日本否认现状**：发言人5指出现在很多日本人不承认南京大屠杀这一事实。
+## 电影真实与虚构的边界
+- **主要人物虚构**：电影中主角与日本军官建立友谊的情节为虚构，但照片拍摄本身真实，只是方式与电影描述不同。
+- **照片来源真实**：真实历史中由两名美国传教士拍摄日军暴行照片；同期中国照片冲洗人员无意间发现日军拍摄的暴行照片（当时属日本禁文），偷偷拷贝藏匿，抗战后提交给国民政府军事法庭作为审判日本战犯的证据。
+- **中华门战斗真实**：电影开头中华门城墙战斗是真实历史细节，对应日军进攻南京时遭遇的抵抗。
+- **挹江门惨案真实**：电影中挹江门撤退场景基于真实事件——宪兵未让平民撤出，守军未收到撤退命令，两方信息差导致惨案发生。
+- **战后审判真实**：电影尾声审判情节属实，打进南京的谷寿夫（第六师团师团长）及多名基层日军军官被枪决。
+## 南京大屠杀的历史成因
+- **日军首次遭迎头痛击**：自1931年九一八事变以来，日军占领东北、华北均未遭遇成规模抵抗；1937年8月13日淞沪抗战是日军入华以来首次遭受迎头痛击，战场惨烈、伤亡惨重。
+- **军纪失控与人性泯灭**：日军从上海追击至南京历时约四个月，缺乏军纪约束、已"杀红眼"，攻破南京后无法律或军纪约束，导致惨无人道的南京大屠杀。
+- **指挥官更替是关键转折**：原指挥官松井石根（老牌皇道派军人）曾发布命令避免烧杀抢掠，因其生病被临时替换；继任者朝香宫鸠彦亲王（裕仁亲王的叔叔）狂热追随脱亚入欧思想，视亚洲其他国家为低贱，上任后发布第一道命令即"不留俘虏"，导致日军军纪彻底失控。
+- **日军心理动因**：从日军视角看，遭受前所未有抵抗产生应激创伤；结合日本历史上攻破城镇后屠城的传统，以及高压武士道精神下的欺凌与霸凌背景，日军以放纵作为宣泄。
+## 国人对抗战历史的关注度
+- **沈阳伪满洲国博物馆**：发言人2上午前往参观，下午已排不上队、必须预约，认为国人对抗战历史关注度高。
+- **唐山大地震纪念馆**：发言人2参观时情况类似，参观者众多。
+- **上海淞沪会战纪念馆**：发言人3参观时下大雨仍人满为患，大人小孩都很多，认为上海在抗战宣传方面做得好。
+- **南京大屠杀纪念馆**：发言人3提到预约困难、很难抢到；发言人4表示多年前去过，当时尚可预约。
 # 金句总结
-&gt; 在战场上长达四个月的一个状态，然后已经杀红眼了，就是可以说是在战争底下那种就是人性的泯灭吧。
-- 讲到日军从上海追击至南京途中军纪失控、攻破南京后发生大屠杀的成因。
-&gt; 从他们当时那样的一个心态来说，就。觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。
-- 分析日军在淞沪会战遭受迎头痛击后，其心态与后续暴行之间的关联。
-&gt; 因为从他自己的角度来说，就是说我兴许我活不到战争结束，那我就趁着我还活着的时候，我对自己进行一种放纵。
-- 解释日军攻破城镇后以屠城进行狂欢与麻痹的心理动因。
-&gt; 从上到下那种高压武士道的精神那种，哦，就是。欺凌与霸凌的这种背景之下，更想找一种宣泄口这种方式来发泄。
-- 剖析高压武士道精神背景下日军寻找宣泄口、最终导致军纪失控。
-&gt; 果然他上任之后发布的第一道命令就是不留俘虏，月后祭坟。
-- 提及朝香宫鸠彦亲王接替松井石根后发布的第一道命令，直接导致南京大屠杀。
+&gt; “从他们当时那样的一个心态来说，觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”
+- 背景：分析日军攻破南京后实施大屠杀的心理动因，结合日本博物馆所见与日军自九一八事变以来首次遭遇迎头痛击的背景。
+&gt; “攻破了敌方的城镇，都要以屠城来进行自己那种狂欢与麻痹。”
+- 背景：解释日本历史传统中屠城行为，作为南京大屠杀发生的历史渊源之一。
+&gt; “从上到下那种高压武士道的精神……更想找一种宣泄口这种方式来发泄。”
+- 背景：论述武士道精神高压下日军寻求宣泄，导致军纪失控并蔓延至对平民的暴行。
+&gt; “在他的眼里，整个亚洲国家除了日本以外，其他国家都是低贱的。”
+- 背景：描述朝香宫鸠彦亲王接任日军统帅后的立场，其上任后发布“不留俘虏”命令。
+&gt; “果然他上任之后发布的第一道命令就是不留俘虏，月后祭坟。”
+- 背景：指出朝香宫鸠彦亲王上任后首道命令直接导致日军格杀无论，最终酿成南京大屠杀。
+&gt; “照片是真实发生的。”
+- 背景：回应电影中照片真实性的讨论，确认照片拍摄为史实，但拍摄方式与电影描述不同。
 # Q&amp;A 环节
-**发言人4**：电影里主角和一名日本军官好像建立了友谊，这个情节是虚构的，还是真有这样的日本军官？
-**发言人1**：电影里的主要人物是虚构的，但照片拍摄是真实的，只是方式与电影描述不同。真实历史是两名美国传教士拍摄了日军暴行；同时期我国一名负责给日本人冲洗照片的人员无意间发现这些照片，偷偷拷贝藏起，抗战后交给国民政府军事法庭，作为审判日本战犯的证据。
-**发言人5**：现在好多日本人还不承认南京大屠杀这件事。
-**发言人1**：对。电影里真实的历史细节包括：开头中华门城墙的战斗是真实的；挹江门撤退时，宪兵没让平民撤出，守军未收到撤退命令，双方信息差导致惨案；电影尾声审判中，谷寿夫等打进南京的部队主犯被枪决，也是真实历史。</t>
+**发言人4**：电影里面虚构的部分，主角一度和一个日本军官建立友谊，这个日本军官是不是真实的？
+**发言人1**：电影里的主要人物是虚构的，但照片的拍摄是真实的，只是不是以电影里描述的方式进行的。真实历史是当时两名美国传教士拍摄了日军暴行；同时期我国一位负责给日本人冲洗照片的人员无意间发现这些暴行照片，在日本属于禁文，他偷偷拷贝藏起来，抗战后递交给国民政府军事法庭，作为审判日本战犯的证据。
+**发言人4**：电影里中华门城墙的战斗是不是真实的？
+**发言人1**：日军进攻南京所遭受的抵抗，开头中华门城墙的战斗是真实历史细节。挹江门撤退时，宪兵没让平民撤出去，守挹江门的部队没收到撤退命令，两边信息差造成最终惨案。电影尾声关于审判，打进南京那几支部队的谷寿夫（第六师团师团长）等几个上了新闻的主犯，基层日军军官当时被枪决，这段也是真实历史。
+**发言人5**：现在好多日本人还不承认这个事情。
+**发言人1**：对，确实是这样。</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4228/2161</t>
+          <t>4228/2304</t>
         </is>
       </c>
     </row>
@@ -16453,39 +16502,45 @@
       <c r="C49" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由主持人发言人1发起，参与者发言人2参与，共两人围绕日本国家概况进行交流。讨论由主持人提出“谈谈日本这个国家的概况、大家对日本的印象和了解”直接引出，无特定前情。议题范围涵盖日本历史与文化、天皇制度、社会结构、旅游与购物体验等。讨论以分享观点为主，未形成统一结论。讨论中提及日本文化经历三次转折（大化改新、明治维新、二战后和平宪法转型），以及广场协议后泡沫经济崩溃催生中古店产业等关键信息。整体推进方式为漫谈发散，由主持人主导讲解，参与者穿插提问与分享，话题从历史文化自然过渡至旅游购物。
+本次会议围绕日本国家概况展开探讨，由主持人（发言人1）引导，发言人2参与，以自由发言形式进行。讨论由主持人提出“日本对中国人印象复杂”的由头切入，涉及日本文化历史阶段、天皇制度与君主立宪、购物旅游体验等议题。整体以分享观点为主，未形成统一结论。讨论按议题逐块推进，从文化历史切入，延伸至政治制度与消费体验。原文关键锚点包括：日本文化三次转型（大化改新、明治维新、和平宪法转型）、1945年麦克阿瑟要求天皇公开露面、广场协议后泡沫经济崩溃催生中古店产业。
 # 发言要点
-## 日本历史与文化
-- **发言人2**：读研时上过日本文化课程，读过老舍《四世同堂》后，认为民族仇恨还是应该要有一点影响。
-- **发言人1**：日本文化缺乏原创，多为外来接收后的本土化改进，经历三次转折——大化改新、明治维新、二战后和平宪法转型。
-- **发言人1**：大化改新后日本向中国和朝鲜半岛学习，在吴越文化基础上本土化转型，形成和服、制茶、漆器等传统印象。
-- **发言人1**：明治维新后日本向欧美列强学习，借鉴英国和德国的法度；二战后美国制定和平宪法，推动社会结构转型，形成动漫、二次元、汽车工业、铁道工业等现代印象。
-- **发言人2**：日本民族性格极端，因其为岛国、气候不稳定，如发展农业可能遭遇海啸等灾害，导致性格容易极端。
-- **发言人1**：古代天皇对各地封建君主而言更像吉祥物般存在，类似东汉末年、战国时期的天子，被供奉为神灵以精神层面控制百姓。
-- **发言人1**：1945年二战结束后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，从精神上打破固有认知以推动社会转型。
-- **发言人1**：日本现为君主立宪制，天皇及皇室成员不能参与政治和国家事务，政治由国会和内阁选出首相执政，体制与英国、西班牙相近；天皇存在感不如英国国王，因英国国王还是英联邦国家名义元首，日本只有本州岛范围。
-## 日本旅游与购物
-- **发言人1**：东京购物和博物馆资源丰富，推荐美妆、护肤品、玩具，如数码宝贝玩偶、铁甲小宝原装及数码宝贝第二部黑暗战路暴龙兽合金版均为秋叶原最早发行。
-- **发言人1**：日本奢侈品便宜，中古店（二手奢侈品商店）很多；中古店源于广场协议后泡沫经济一夜崩溃，失业上班族寄卖高档大衣、西装、皮具等催生新产业。
-- **发言人1**：中古店在上海很多，可买到LV、Burberry、古奇等上个世纪知名大牌，女性款式较多，男性款式相对有限。
-- **发言人1**：个人偏好镰仓气候，夏天去比较舒服，喜欢登山、爬富士山、逛古城和博物馆，如镰仓、京都、名古屋等关西地区有本土化改良的文化场景。
+## 日本文化历史阶段
+- **发言人2**：读研时上过讲日本文化的课，读过老舍《四世同堂》后，认为民族仇恨还是应该要有一点影响；同时觉得日本文化对中国影响挺多。
+- **发言人1**：日本文化没有原创，都是外来接收后的本土化改进转型，追问发言人2所指具体是哪个历史阶段的日本文化。
+- **发言人2**：既指传统文化（漆艺、制茶茶艺），也指现代文化艺术。
+- **发言人1**：漆器和茶艺都源自唐朝，在吴越文化基础上本土化转型；日本文化经历三次转折——大化改新、明治维新、二战后和平宪法转型。
+- **发言人1**：大化改新后大规模向中国和朝鲜半岛学习，形成和服、制茶、漆器等传统印象；明治维新后向欧美列强看齐，引入英国和德国的法度；二战后美国制定和平宪法，社会结构大规模转型，同时期积极向美国看齐。
+- **发言人1**：现代日本给我们的印象中，动漫、二次元、汽车工业和铁道工业影响功不可没。
+## 天皇制度与君主立宪
+- **发言人2**：听过一种评论——日本是岛国、气候不稳定，农业可能因海啸等灾害毁于一旦，所以民族性格容易极端。
+- **发言人1**：古代天皇对各地封建君主而言更像吉祥物般的存在，类似东汉末年、战国时期的天子，不能退位，被当作神灵供奉，以此在精神层面控制老百姓。
+- **发言人1**：1945年二战结束后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，从精神上打破固有认知，推动日本社会转型。
+- **发言人2**：询问现在日本民众对天皇是否还有崇拜。
+- **发言人1**：没有了，现在类似英国、西班牙的君主立宪制，天皇是象征性存在，不能参与政治和国家事务，由国会和内阁选出首相执政；美国把日本改造成英美海洋法系的国家结构。
+- **发言人1**：日本天皇影响力不如英国国王，因为英国国王还是整个英联邦国家的名义元首（澳大利亚、新西兰、加拿大等），日本只有本州岛范围，天皇没有任何实权，靠政府养着。
+- **发言人1**：君主立宪制国家除日本、英国外，欧洲还有西班牙等；东南亚有泰国；教皇属于宗教领域，不属于国家体制。
+## 日本购物与旅游
+- **发言人1**：推荐东京、大阪等城市，东京有美食、购物、博物馆；秋叶原是动漫周边发源地，数码宝贝玩偶、铁甲小宝原装、黑暗战路暴龙兽合金版都是秋叶原最早发行。
+- **发言人1**：日本购物值得买的有化妆品、护肤品、玩具、奢侈品；中古店（二手奢侈品商店）源于广场协议后泡沫经济一夜崩溃，失业上班族将高档大衣、西装、皮具皮鞋等寄卖，催生新产业。
+- **发言人1**：中古店在上海有很多，能买到上个世纪LV、Burberry、古奇等大牌，女性款式多，男性款式相对少、范围有限。
+- **发言人1**：去日本最喜欢爬山（富士山）、看古城、逛博物馆，推荐镰仓、京都、名古屋关西一带；镰仓夏天气候比较舒服。
 # 共识形成
-- **一致意见**：双方均认可日本文化对当代影响深远，且其文化缺乏原创性，多为外来接收后的本土化改进；对日本旅游与购物体验评价较高，认为其在服务业与购物体验方面首屈一指。
-- **倾向性认识**：发言人1系统梳理日本文化三次转折——大化改新、明治维新、二战后和平宪法转型，并指出天皇制度从古代「吉祥物」式存在，经麦克阿瑟1945年要求天皇公开露面后，转变为无实权的象征性君主立宪制，与英国、西班牙体制相近；发言人2认同此框架，并补充认为日本民族性格极端与岛国气候不稳定有关。
-- **主要分歧点**：发言人2提出「民族仇恨还是应该要有一点影响」，发言人1回应称中日民族仇恨「没那么严重」，并对比欧洲、中亚民族仇恨更为严峻——双方对历史仇恨在当代认知中的权重存在不同侧重，未就此达成统一结论。
+- **一致意见**：日本文化缺乏原创，属于外来接收后的本土化转型，经历三次转折——大化改新（向中国、朝鲜半岛学习，形成和服、制茶、漆器等传统）、明治维新（向欧美学习，引入英国和德国的法度）、二战后和平宪法转型（美国主导，社会结构转型，向美国看齐）。现代日本文化标志包括动漫、二次元、汽车工业和铁道工业。
+- **倾向性认识**：天皇在古代对各地封建君主而言是吉祥物般的存在；1945年二战后麦克阿瑟要求天皇公开露面，打破其神格，天皇成为象征性存在，不能参与政治，由国会和内阁选出首相执政。与英国国王相比，日本天皇影响力较小，因英国国王是英联邦名义元首；君主立宪制国家还包括西班牙、泰国等。
+- **主要分歧点**：发言人2提出「日本民众现在对天皇是否还有崇拜」的疑问，发言人1回应称已无崇拜，天皇是象征性存在；但发言人2未明确接受该结论，此问题未完全定论。
 # 待探讨问题与后续
-- **未确认**：日本民众现在对天皇是否仍有崇拜，发言人2提出该疑问，发言人1回应称已无崇拜、天皇为象征性存在，但未提供调查数据或民意依据。
-- **未确认**：二次元一词的英文表达，发言人1现场提问，未获明确回答，讨论随即转向其他话题。
-- **未定论**：日本民族性格与岛国气候不稳定之间的因果关系，发言人2提出该观点，发言人1未作回应或补充，该话题未深入展开。
-- **未定论**：日本文化缺乏原创性、多为外来接收后本土化改进的判断，发言人1提出此观点，发言人2未明确赞同或反对，讨论未就此形成一致认识。</t>
+- **未确认**：日本民众现在对天皇是否还有崇拜。发言人2提出此疑问，发言人1回应称天皇已无实权、为象征性存在，但未就民众当前的实际崇拜程度给出明确结论。
+- **未定论**：日本文化具体指哪一个历史阶段的文化。发言人2提及喜欢日本传统文化（漆艺、茶艺）与现代文化艺术，发言人1追问其具体所指的历史阶段，发言人2未作明确界定，讨论随即转向文化转型的宏观梳理。
+- **未定论**：日本民族性格是否因其岛国地理与不稳定气候而趋于极端。发言人2转述一种评论，认为日本民族性格极端与岛国气候不稳定有关，发言人1未直接回应此观点，话题转向天皇制度，该判断未获进一步讨论或确认。
+- **未提及**：原文未涉及任何后续分工、跟进事项或下次会议的约定。</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>31.8</v>
+        <v>37.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4892/1784</t>
+          <t>4892/2179</t>
         </is>
       </c>
     </row>
@@ -16698,58 +16753,62 @@
       <c r="C50" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议为自由文学讨论，由发言人1提议从《西游记》延伸至《三国演义》，共5位发言人参与。讨论以三国历史细节、人物评价与阵营偏好为起点，随后转向《红楼梦》的版本、判词与人物命运。三国部分围绕诸葛亮去世后的正史后续（姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴）、赤壁印象、蜀汉阵营偏好、刘备称汉中王引发的连锁反应（吕蒙白衣渡江、夷陵惨败）、借荆州与湘水划界、单刀赴会、东吴大都督结局、魏延烧栈道及三顾茅庐与隆中对等议题展开；红楼梦部分则聚焦前八十回与后四十回作者差异、第五回判词预示结局、晴雯与袭人的人物对应、林黛玉与薛宝钗的明清解读及秦可卿前朝公主之说。讨论以分享观点为主，未形成统一结论，整体按三国、红楼梦两大议题逐块推进，发言人多以补充史实与解读的方式参与，穿插个别成员的提问与回应。
+本次讨论由发言人1提议，从先前《西游记》话题延伸至《三国演义》与《红楼梦》，共5位成员（发言人1至发言人5）参与，属自由漫谈式文学交流。三国部分围绕历史细节与人物评价展开，涉及赤壁之战、阵营偏好、刘备称汉中王引发的连锁反应（吕蒙白衣渡江、夷陵惨败）、借荆州与湘水划界、单刀赴会、东吴大都督结局、魏延烧栈道及三顾茅庐与隆中对等议题；红楼梦部分聚焦版本差异（前八十回与后四十回作者问题）、第五回判词预示结局、人物命运解读（晴雯为黛玉替身、袭人似宝钗）及反清复明等索隐观点。讨论以分享观点为主，未形成统一结论，由发言人1主导引导话题，成员轮流发言，整体呈逐议题推进但发散延伸的特点。
 # 发言要点
 ## 三国印象与历史细节讨论
 - **发言人2**：三国到诸葛亮去世就基本差不多了，后面没意思，自己没看完；印象最深刻的章节是赤壁，认为三国前面比后面有意思。
-- **发言人2**：受《三国演义》影响，偏好蜀汉刘备阵营，理由是刘备白手起家。
-- **发言人1**：正史后续还有姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴等事件；孙权晚年昏庸，在二宫之争中害死两个儿子，导致东吴朝廷大乱。
-- **发言人1**：刘备称汉中王不妥，引发连锁反应——吕蒙白衣渡江、刘备伐吴失败（夷陵惨败）；若未称王，孙权可能不会彻底决裂。
-- **发言人1**：讲述借荆州与湘水划界细节——孙权只要求刘备归还部分地区，刘备不乐意，孙权派兵强夺荆南三郡；因曹操攻下汉中威胁西川，刘备回师并与孙权签订湘水之盟。
+- **发言人2**：受《三国演义》影响，偏好蜀汉刘备阵营，理由是刘备算白手起家。
+- **发言人1**：正史后续还有姜维北伐、孙权二宫之争（晚年昏庸害死两个儿子致东吴朝廷大乱）、邓艾偷渡阴平、姜维反间计同归于尽、刘禅投降、西晋灭吴。
+- **发言人1**：刘备称汉中王在封建礼治时期有不妥之处，引发连锁反应——吕蒙白衣渡江、刘备伐吴失败（夷陵惨败）。
+- **发言人1**：借荆州一事，孙权只要求刘备归还部分地区，刘备不乐意；孙权第一次派兵强夺荆南三郡，刘备集结大军准备进攻东吴，后因曹操攻下汉中而回师，与孙权签订湘水划界（湘水之盟）。
 - **发言人1**：单刀赴会实为鲁肃与关羽各带随从在中立区谈判，被罗贯中美化为关云长只身赴险。
-- **发言人2**：白衣渡江伪装成商人，在古代打仗不太道德、突破底线，开了坏头，吕蒙口碑不好。
-- **发言人1**：吕蒙白衣渡江偷盟友家，后世把「小偷鼠辈」与吕蒙名字画等号。
-- **发言人1**：东吴大都督结局——周瑜被曹人射毒箭阵亡，鲁肃得瘟疫病故，吕蒙病故，陆逊在二宫之争时被孙权活活逼死。
-- **发言人1**：陆逊因责备孙权立太子后不应让两子争斗，被孙权逼迫而死。
-- **发言人2**：蜀汉也内斗；对陆逊的印象主要来自三国杀，东吴后期政治斗争严重，大都督们没太闹好。
-- **发言人1**：刘禅自知能力不行，完全放权给诸葛亮；诸葛亮去世后姜维无力回天，刘禅轻信黄皓谗言；姜维是魏国降将，若非诸葛亮提拔没有说服力，众人不服他。
-- **发言人1**：魏延正史没有谋反，只是不甘心大军撤退，烧毁悬崖栈道；若非姜维断后挡住司马懿军队，后果不堪设想——无反心但行为与谋反无异，实为与杨仪的个人矛盾上升至国家层面。
-- **发言人5**：三顾茅庐——刘备中原屡战屡败，深感缺乏谋士，经人推荐得知隆中诸葛亮有卧龙之才，携关羽、张飞三次拜访，前两次未见到，第三次诸葛亮被其打动，提出隆中对战略（联合孙权），最终同意辅佐刘备。
-- **发言人1**：隆中对战略为横跨荆益、外结好孙权、西和诸戎，趁魏国变动时北伐；白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，与结好孙权相矛盾。
-- **发言人1**：诸葛亮北伐目标在关中平原和陇西（今陕西、甘肃南部），希望纵跨凉益以图中原；第一次北伐赢面大，因马谡兵败街亭而破产，后期只能拖延魏国灭蜀时间，北伐更像绝望中的抗争。
+- **发言人1**：刘备不还荆州把孙刘联盟信任耗尽；孙权打不下合肥，索性偷袭荆州、袭关羽。
+- **发言人2**：白衣渡江伪装成商人，在古代打仗突破底线、口碑不好，开了坏头。
+- **发言人1**：吕蒙白衣渡江开坏头，后世把「小偷鼠辈」与吕蒙名字画等号。
+- **发言人2**：对陆逊印象只剩火烧连营，东吴后期政治斗争严重，几个大都督内斗得厉害。
+- **发言人1**：东吴大都督结局——周瑜被曹人射毒箭阵亡，鲁肃得瘟疫病故，吕蒙病故，陆逊在二宫之争时被孙权活活逼死（因问责孙权立太子后不该让两子相争）。
+- **发言人2**：蜀汉也内斗，魏延也是被砍的。
+- **发言人1**：刘禅自知能力不行，完全放权给诸葛亮；诸葛亮去世后姜维无力回天，刘禅轻信黄皓谗言，且姜维是魏国降将、若非诸葛亮提拔没有说服力，众人不服他。
+- **发言人1**：魏延正史上没有谋反，只是不甘心大军撤退，烧了悬崖边栈道；若非姜维断后挡住司马懿军队，后果不堪设想——无反心但行为与谋反无异，实为与杨仪个人矛盾上升至国家军队层面。
+- **发言人5**：三顾茅庐——刘备中原屡战屡败、深感缺乏谋士，经人推荐得知隆中诸葛亮有卧龙之才，携关羽、张飞三次前往：第一次诸葛亮外出，第二次恰逢风雪，第三次终于见到，诸葛亮被打动并提出隆中对战略（联合孙权），最终同意辅佐刘备。
+- **发言人1**：隆中对战略为横跨荆益、外结好孙权、西和诸戎，趁魏国有变北伐；白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，与结好孙权相矛盾。
+- **发言人1**：诸葛亮北伐目标在关中平原和陇西（今陕西、甘肃南部），希望纵跨凉益以图中原；第一次北伐赢面大，因马谡兵败街亭而破产，后期只能拖延魏国灭蜀时间，诸葛亮与姜维北伐更像绝望中的抗争。
 ## 红楼梦版本与人物讨论
 - **发言人4**：红楼梦可当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在是没有解开的谜底。
 - **发言人3**：红楼梦只写了前八十回，后面是别人续写的。
-- **发言人2**：有反清复明的版本解读，真正的意义估计与当时朝代、社会有关。
-- **发言人4**：第一遍读高鹗续写版本时觉得挺合理，年纪小不知道后四十回不是同一作者；反复读前八十回后再接触续写，发现林黛玉性格变了很多。
-- **发言人3**：第五回贾宝玉梦游太虚幻境，判词已把结局交代了。
-- **发言人4**：判词没有点得那么明确，探春、史湘云的结局都是猜的，最后谁和贾宝玉在一起也没说清。
-- **发言人4**：晴雯是林黛玉的替身，性格像林黛玉；袭人性格像薛宝钗；晴雯之死是曹雪芹原作所写，映照后面情节。
-- **发言人2**：有解读说林黛玉代表明朝、薛宝钗代表清朝。
-- **发言人4**：有人解读秦可卿是前朝公主；秦可卿是金陵十二钗正钗之一，可惜老早去世。
-- **发言人4**：第五回贾宝玉在秦可卿床上睡觉做梦到太虚幻境，看到判词——十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每个人命运。
-- **发言人2**：疑问为何选高鹗后四十回作为官方结尾。
-- **发言人4**：高鹗续写总体比较合理，官方说法是在残稿上梳理完善，未违背作者原意，但诗词能力不及曹雪芹。
-- **发言人3**：北京植物园旁边村子有曹雪芹小道，之前爬山看到过。
-- **发言人4**：北京植物园里有曹雪芹的故居。
+- **发言人2**：提到有反清复明的版本解读，认为真正意义与当时朝代、社会有关。
+- **发言人4**：第一遍读高鹗续的后四十回时觉得挺合理，当时不知道后四十回不是同一作者；把前八十回反复读后再接触续作，会发现林黛玉性格变了很多。
+- **发言人3**：第五回贾宝玉梦游太虚幻境，已用判词形式把结局交代了。
+- **发言人4**：判词没有点得那么明确，探春、史湘云的结局都是猜的，最后谁和贾宝玉在一起也说不准。
+- **发言人5**：问为什么会有悲剧——贾宝玉与林黛玉真心相爱却被迫娶了薛宝钗。
+- **发言人4**：林黛玉死是后四十回内容、非原作所写，但原作意图肯定是悲剧。
+- **发言人4**：晴雯是林黛玉的替身（性格像林黛玉），袭人性格像薛宝钗；晴雯之死是曹雪芹原笔，映照后面命运。
+- **发言人2**：看到解读说林黛玉代表明朝、薛宝钗代表清朝。
+- **发言人4**：还有解读说秦可卿是前朝公主；秦可卿是金陵十二钗正钗之一，可惜老早去世。
+- **发言人4**：第五回贾宝玉在秦可卿床上睡觉做梦到太虚幻境，看到判词——十二金钗分正钗（小姐）与副钗（丫鬟），判词对应每个人命运。
+- **发言人2**：问为何选高鹗后四十回作为官方结尾。
+- **发言人4**：高鹗续作总体比较合理，官方说法是在残稿上梳理完善、未违背作者原意，但写作细节和诗词能力不及曹雪芹。
+- **发言人3**：北京植物园（北苑所）旁边村子有曹雪芹小道，之前爬山看到过。
+- **发言人4**：北京植物园里面有曹雪芹的故居（工具）。
 # 共识形成
-- **一致意见**：与会者普遍认为《三国演义》前半部比后半部更有意思，发言人2明确表示「三国到诸葛亮去世也基本就差不多了」，此观点未遭反驳；对吕蒙白衣渡江一事，发言人1与发言人2均认为其「开了个坏头」「突破底线」，吕蒙因此在后世口碑不佳。
-- **倾向性认识**：发言人2受演义影响偏好蜀汉刘备阵营，认为刘备「白手起家」；发言人1则指出刘备称汉中王引发连锁反应，导致吕蒙白衣渡江、夷陵惨败，双方对刘备评价侧重不同但未正面交锋。关于魏延，发言人1主张其「没有反心，但他的行为跟谋反没什么实质上的区别」，因烧毁栈道危及大军撤退。
-- **主要分歧点**：发言人2认为白衣渡江是「古代打仗比较不太道德，突破底线」；发言人1补充吕蒙因此被后世与「小偷鼠辈」画等号，二人一致。对《红楼梦》后四十回，发言人4认为高鹗续写版本「总体来说还是比较合理」，官方说法「没有违背作者原意」；发言人2则对续写结局表示「没看明白他到底是想说啥」，对合理性存疑，双方未就此达成统一。
+- **一致意见**：三国部分，发言人2与发言人1均认为**诸葛亮去世后三国故事基本结束**，后续内容无趣；对**白衣渡江**，发言人2与发言人1一致认为吕蒙伪装商人偷袭盟友突破底线、开了坏头，导致吕蒙后世口碑不佳。红楼梦部分，发言人3与发言人4一致确认**前八十回为曹雪芹所写、后四十回为他人续写**，且第五回判词已预示结局。
+- **倾向性认识**：发言人2受《三国演义》影响偏好蜀汉刘备阵营，认为刘备白手起家；发言人1补充正史视角，认为刘备称汉中王引发连锁反应（吕蒙白衣渡江、夷陵惨败），并指出东吴大都督结局多不佳（周瑜中箭阵亡、鲁肃病故、吕蒙病故、陆逊被孙权逼死）。红楼梦部分，发言人4认为高鹗续的后四十回总体合理，官方说法未违背作者原意；发言人2提及林黛玉代表明朝、薛宝钗代表清朝的反清复明解读。
+- **主要分歧点**：对魏延评价，发言人1认为魏延无谋反之心，但烧栈道行为与谋反无异；发言人2仅提及魏延被砍，未作评价。对刘备评价，发言人2认可其白手起家，发言人1则强调其称王决策不当引发连锁反应。红楼梦结局归属，发言人4认为探春、史湘云结局为猜测，未明确；发言人2对后四十回合理性存疑，但未明确反对。
 # 待探讨问题与后续
-- **未确认：** 红楼梦后四十回是否为高鹗续写及其官方定本地位，发言人2对高鹗续本为何成为官方结尾提出疑问，发言人4回应称官方说法是依据残稿梳理完善、未违背作者原意，但发言人2仍表示「没看明白他到底是想说啥」。
-- **未定论：** 探春、史湘云等人物结局仅凭判词无法明确，发言人4指出「都是猜的」，未有人能确切说出最终谁与贾宝玉在一起。
-- **未确认：** 红楼梦存在「反清复明」版本解读，发言人2提及林黛玉、薛宝钗分别代表明朝与清朝的说法，发言人4补充秦可卿被解读为前朝公主，均属民间解读、未获证实。
-- **待核实：** 北京植物园附近存在「曹雪芹小道」，发言人3称在北苑所旁边村子爬山时见过，发言人2提及植物园内有曹雪芹故居，具体位置与史实依据未进一步核实。
-- **未定论：** 三国部分对刘备称汉中王是否引发孙刘决裂存在不同看法，发言人1认为称王不妥引发连锁反应，发言人2未明确表态，仅表示受演义影响偏好蜀汉阵营。</t>
+- **未确认：** 红楼梦后四十回是否为高鹗所续、官方版本是否未违背曹雪芹原意——发言人4认为高鹗续本总体合理、官方说法称未违背作者原意，但发言人2对续本结局合理性存疑，表示「没看明白他到底是想说啥」，未达成一致。
+- **未定论：** 红楼梦探春、史湘云的结局以及最终谁与贾宝玉在一起——发言人4指出判词未点明，这些结局「都是猜的」，无人能说清。
+- **未确认：** 红楼梦「反清复明」解读——发言人2提及有人解读林黛玉代表明朝、薛宝钗代表清朝，发言人4补充有解读称秦可卿是前朝公主，均属流传说法，未获证实。
+- **待核实：** 曹雪芹小道的位置——发言人2称曾去过一个有「曹雪芹小道」的地方，发言人3回应在北京植物园附近、北苑所旁边的村子见过，发言人4提到植物园内有曹雪芹故居，具体位置未核实。
+- **未定论：** 三国后续情节——发言人2表示诸葛亮去世后未再看完，不知后面内容；发言人1补充了姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴等正史脉络，但未继续展开讨论。
+- **未确认：** 魏延是否谋反——发言人1认为魏延无谋反之心，但烧毁栈道的行为「跟谋反没什么实质上的区别」，此判断为个人观点，未获他人回应或反驳。</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>47.3</v>
+        <v>50.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6453/2967</t>
+          <t>6453/3254</t>
         </is>
       </c>
     </row>
@@ -16866,49 +16925,52 @@
       <c r="C51" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由发言人1发起，延续此前《红楼梦》《三国》《水浒》《西游记》《金瓶梅》的系列话题，从兵法和战法角度切入三国战役。成员共3人，按原文编号为发言人1、发言人2、发言人3。讨论围绕赤壁之战与合肥之战的影响、火烧连营与陆逊评价、孙权军事能力与蜀汉武将评价三大议题展开。发言人1系统分析了曹操因以骑兵为主、缺乏水军而败于赤壁，东吴北伐必经合肥而孙权一生未能攻克，并详述公元215年合肥之战中张辽率800死士大败孙权十万大军的过程；随后讲述刘备在夷陵之战因体恤下属在密林扎营，被陆逊抓住秋季干燥时机火攻、连营七百里被烧的经过。发言人2对孙权评价表示前后反差，发言人3补充孙权早期败仗及蜀汉武将看法。整体以分享观点为主，未形成统一结论，对孙权军事能力评价偏负面，对关羽战力认可度较高。讨论按议题逐块推进，由发言人1主导讲述，其余成员补充与回应，并延伸至北伐路线与街亭之战假设。
+本次讨论围绕三国时期赤壁之战、合肥之战、火烧连营等战役展开，从兵法和战法角度分析各方军事特点与将领能力。成员共3人（发言人1、发言人2、发言人3），由发言人1主导推进，延续此前《红楼梦》《三国》《水浒》《西游记》《金瓶梅》的系列讨论，延伸至三国故事线的军事议题。议题范围包括：赤壁之战的影响、合肥之战与孙权北伐、火烧连营与陆逊、三国人物评价（孙权、刘备、关羽、张飞、五子良将）、诸葛亮北伐的假设性探讨。讨论以分享观点为主，未形成统一结论，整体倾向认为赤壁之战与合肥之战均因双方擅长领域不同而僵持，孙权北伐始终未能突破合肥，后人称其为“合肥战神孙十万”。关键锚点包括公元215年合肥之战、张辽率800死士大败孙权十万大军、火烧连营七百里。讨论按议题逐块推进，由发言人1提出话题并讲述史实，发言人2、发言人3穿插回应与补充，整体呈漫谈发散式推进。
 # 发言要点
-## 赤壁之战与合肥之战的影响
-- **发言人1**：赤壁之战曹操失败主因是军队以虎豹骑等骑兵为主、擅长陆战，刚收服荆州没有像样水军，面对长江如同渡海攻坚战，过不去长江；东吴则以水军为主，双方各有所长。
-- **发言人1**：东吴北伐必经合肥——从建业（今南京）过长江到江北，经小河到巢湖上岸，打下合肥后才能靠近淮河，再连徐州、鲁西南乃至海河一带；孙权一生多次攻合肥均未攻克。
-- **发言人1**：公元215年合肥之战，曹军主力在攻汉中，合肥仅张辽、李典、乐进三将镇守且三人矛盾深（张辽原属吕布）；张辽率800死士骑马冲阵，大败孙权十万大军，留下「张八百大破孙十万」的段子。
-- **发言人1**：合肥之战中孙权在城外扎营准备攻城，张辽突袭时吴军未及反应；张辽战后询问俘虏，得知骑术好、箭法准、上身长下身短、留小胡子的逃跑者就是孙权，后悔差点将其擒获。
-- **发言人1**：合肥城内张辽跺两脚连小孩都不敢啼哭；后人吐槽孙权「正面打不过、偷盟友家专业」，南京紫金山孙权墓确切位置已失，碑前堆满张辽的影视海报和游戏卡片。
-- **发言人2**：小时候看「生子当如孙仲谋」觉得孙权厉害，长大后观感反转，认为其评价偏负面。
-- **发言人3**：孙权在孙十万之前也打过败仗，几万人被对方几千人追着打，对手可能是刘繇或类似人物，但具体是谁记不清。
-- **发言人1**：曹操说「生子当如孙仲谋」是因为孙策传位给孙权，孙权开疆拓土不行但能守住家业，对比曹操诸子算争气的。
-## 火烧连营与陆逊评价
-- **发言人1**：夷陵之战刘备体恤下属，不忍酷暑折磨让士兵在密林扎营避暑；陆逊抓住秋季干燥、树叶飘落的时机放火，连营七百里被烧光，刘备只身逃回白帝城。
-- **发言人2**：问陆逊是否与孙家有仇，陆家和孙家没听过有仇。
-- **发言人1**：陆逊是江东四杰之一；孙策因是外来户、行事冒失被称为「小霸王」，后被刺杀。
-## 孙权军事能力与蜀汉武将评价
-- **发言人3**：从南往北打的成功案例除朱元璋外不好找，多数能守住首都就不错，暗指南北作战方向差异。
-- **发言人1**：夷陵之战刘备被仇恨冲昏头脑而冒进；汉中之战有法正、黄权辅佐，靠地势地利把曹操耗出汉中，打得还行。
-- **发言人1**：论打仗关羽很厉害，水淹七军之外还有阵中斩将——斩颜良、诛文丑，是历史上第一个阵中斩将直接改变战场局势的人。
-- **发言人3**：关羽个人战力强，但水淹七军之外想不起其他部队作战战绩。
-- **发言人1**：黄忠定军山阵斩夏侯渊，但可能与关羽不同，关羽是摆好阵后斩将，黄忠像是从山上冲下来。
-- **发言人3**：张飞想不起经典战役，只知道长坂坡。
-- **发言人1**：演义里张飞与马超在成都城下大战五百回合。
-- **发言人3**：正式打仗列阵交锋方面，五子良将（张辽、曹仁、夏侯渊、张郃、徐晃、于禁）战力受认可，张辽是从吕布降过来的。
-- **发言人1**：曹操兵多血厚耗得起；若诸葛亮第一次北伐用魏延守街亭，大概率能反杀张郃，不会像马谡那样轻易丢掉街亭，北伐可能成功；但魏延想法大胆，不符合蜀汉实际支撑。
-- **发言人3**：蜀汉地盘太小，支撑不起魏延的冒险打法。
+## 赤壁之战与合肥之战
+- **发言人1**：赤壁之战曹操失败主因是军队以虎豹骑为主、擅长陆战，刚收服荆州没有像样水军，不敌江东水军；长江过不去，相当于渡海攻坚战、两栖登陆的规格。
+- **发言人1**：东吴北伐必须过合肥——从建业（今南京）过长江到江北，经小河到巢湖上岸，打下合肥才能靠近淮河，再连徐州、鲁西南直至海河一带；孙权一生都在打合肥，始终未攻克。
+- **发言人1**：公元215年合肥之战，曹军主力在攻汉中，合肥仅张辽、李典、乐进三将镇守且三人矛盾深（张辽原属吕布）；张辽率800死士骑马冲阵，大败孙权，留下「张八百大破孙十万」的段子。
+- **发言人1**：孙权在合肥城外扎营准备攻城时，张辽率800死士突袭，吴军未及反应；张辽战后问被俘吴军「马骑得好、箭射得准、上身长下身短、留小胡子的人是谁」，得知是孙权后后悔差点抓住他。
+- **发言人1**：合肥城内张辽跺两脚连小孩都不敢啼哭；后人吐槽孙权「正面打不过、偷盟友家专业」，称其「合肥战神孙十万」；今南京紫金山孙权墓确切位置已失，碑前堆满张辽的影视海报和游戏卡片。
+- **发言人1**：赤壁之战与合肥之战本质相同——曹军骑兵在北方平原作战，遇大江大河无法施展；吴军擅长划船、摇橹、水战，上岸面对虎豹骑毫无应对之策，双方僵持不下。
+- **发言人2**：小时候看「生子当如孙仲谋」觉得孙权厉害，长大后观感反转，认为他不只是「孙十万」的问题。
+- **发言人3**：孙权在孙策刚死时打一个叫「刘油/刘有」的人，几万人被人家几千人追着打，打得挺惨；具体人物未确认（非刘表、非张辽，在赤壁之战前）。
+## 火烧连营与陆逊
+- **发言人1**：刘备体恤下属，不忍酷暑折磨，让士兵在密林扎营避暑；陆逊抓住秋季干燥、树叶飘落的时机，在秋老虎时期放火，连营七百里营地被烧光，刘备只身逃回白帝城。
+- **发言人2**：质疑陆逊是否与孙家有仇，称「陆家和孙家没听过」。
+- **发言人1**：陆逊是江东四杰之一；孙策、孙坚是外来户，孙策被称为「小霸王」、过于冒失，后被刺杀。
+- **发言人1**：曹操说「生子当如孙仲谋」，因孙策传位给弟弟孙权，孙权开疆拓土能力不行但能守住家业，对比曹操几个儿子算最争气的。
+## 三国人物评价
+- **发言人3**：从南往北打（北伐）除朱元璋外不太好找，能守住首都就不错了。
+- **发言人1**：认同北伐难、南下容易。
+- **发言人3**：孙权打仗确实不好，打得都挺颓；刘备至少汉中之战打得挺好。
+- **发言人1**：刘备夷陵之战（火烧连营）被仇恨冲昏头脑、冒进；汉中之战靠法正和黄权辅佐、凭地势地利把曹操耗出汉中，勉强打赢。
+- **发言人1**：论打仗关羽很厉害，水淹七军之外还有阵中斩将（斩颜良、诛文丑），是历史第一个阵中斩将直接改变战场局势的人；失败是阵营内队友不争气，不是能力不行。
+- **发言人3**：关羽个人战力强，但阵中斩将属个人战力而非部队作战；黄忠阵斩夏侯渊与关羽不同，关羽是摆好阵后斩将，黄忠可能是从山上冲下来。
+- **发言人3**：张飞没有经典战役，只知道长坂坡。
+- **发言人1**：张飞在演义里与马超在成都城下大战五百回合。
+- **发言人1**：曹操手下五子良将包括张辽（从吕布降来）、曹仁、夏侯渊、张郃、徐晃、于禁；于禁后来被关羽生擒；曹操血厚人多，耗得起。
+## 诸葛亮北伐假设
+- **发言人1**：若诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，不会像马谡那样轻易丢掉街亭，北伐第一次可能成功；魏延想法大胆，但不符合蜀汉当时的实际支撑。
+- **发言人3**：蜀汉地盘太小。
 # 共识形成
-- **一致意见**：赤壁之战与合肥之战均体现水军与骑兵的作战差异——曹操因以骑兵为主、缺乏水军而败于赤壁；东吴北伐必经合肥，孙权一生未能攻克，公元215年合肥之战中张辽率800死士大败孙权十万大军，孙权本人险被俘虏。与会者认同孙权军事能力评价偏负面，认为其守成有余、开疆不足。
-- **倾向性认识**：对蜀汉武将战力，发言人1与发言人3倾向认可关羽，认为其有阵中斩将战绩（斩颜良、诛文丑），黄忠定军山阵斩夏侯渊亦获认可；张飞缺乏经典战役，仅知长坂坡。发言人1提出若魏延守街亭可能反杀张郃，但魏延想法不符合蜀汉实际，发言人3以「地盘太小了」表示认同。
-- **主要分歧点**：发言人3提及孙权在孙策刚死时曾以数万人被几千人追打，但具体对手与战役名称未能确认，发言人1先后猜测刘表、张辽、曹仁、刘琦等均被发言人3否定，该战役细节未定论。
+- **一致意见**：赤壁之战与合肥之战均因双方各自擅长领域不同而僵持——曹操军队以虎豹骑为主、擅长陆战，因缺乏水军而在赤壁战败；东吴水军擅长水战，但北伐必须经过合肥，上岸后无法与曹军陆战抗衡。发言人1与发言人3均认可孙权打仗能力不佳，发言人3补充孙权在孙策刚死时也曾以数万人被对方几千人追打。
+- **倾向性认识**：对孙权评价形成「守成有余、开疆不足」的倾向——发言人1引曹操「生子当如孙仲谋」说明孙权能守住家业，但一生多次攻打合肥未成功，公元215年合肥之战中张辽率800死士大败孙权十万大军，孙权本人差点被俘，后人称其为「合肥战神孙十万」。
+- **主要分歧点**：关于关羽军事能力，发言人1认为关羽个人战力突出，曾阵中斩将、直接改变战场局势，水淹七军之外还有斩颜良、诛文丑；发言人3质疑关羽除水淹七军外缺乏战绩，认为阵中斩将属个人战力而非部队作战。关于张飞，发言人1提及演义中与马超大战五百回合，发言人3表示不知其经典战役、仅知长坂坡。
+- **未统一结论**：诸葛亮北伐假设——发言人1提出若第一次北伐用魏延守街亭，可能反杀张郃、避免街亭丢失，北伐可能成功，但魏延想法大胆不符合蜀汉实际支撑；发言人3认为蜀汉地盘太小，未就此达成一致。
 # 待探讨问题与后续
-- **未确认**：发言人3提到的孙权早期败仗的具体对手和战役未确认，其仅描述为「孙策刚死的时候」、对手「不是刘表」、在张辽之前，发言人1先后猜测「刘琦时期」「曹仁时期」均未获确认。
-- **未定论**：关于关羽阵中斩将是否为「历史第一人做到」的讨论未达成定论，发言人3提出此说法，发言人1以黄忠定军山阵斩夏侯渊作对比，发言人3认为两者情况不同（关羽为摆好阵后斩将，黄忠可能为从山上冲下），但未进一步核实。
-- **未定论**：若诸葛亮第一次北伐时以魏延守街亭能否反杀张郃、北伐能否成功，仅为发言人1的假设性判断，发言人3仅回应「这地盘太小了」，未展开讨论。
-- **未确认**：发言人3提及孙权早期另有一场「几万人被几千人追着打」的败仗，但对手姓名（「刘油」「刘有」等）始终未能回忆确认。</t>
+- **未确认**：发言人3提到的孙权早期被某人打败的具体人物未确认，发言人3仅记得是孙策刚死时期、赤壁之战前，对方多次打败孙权，但记不清名字，发言人与发言人1先后猜测刘表、张辽、曹仁、刘琦等均未获确认。
+- **未定论**：关羽与黄忠阵中斩将的含金量对比未达成一致，发言人3认为关羽是摆好阵后阵中斩将、直接改变战场局势，黄忠斩夏侯渊可能系从山上冲下，与关羽情况不同，但未深入展开。
+- **未定论**：若诸葛亮第一次北伐用魏延守街亭能否成功的假设未深入讨论，发言人1认为大概率能反杀张郃、北伐可能成功，但魏延想法不符合蜀汉实际支撑，发言人3仅回应「地盘太小」，未继续展开。</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>40.7</v>
+        <v>44.7</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4899/2473</t>
+          <t>4899/2742</t>
         </is>
       </c>
     </row>
@@ -16971,61 +17033,52 @@
       <c r="C52" t="inlineStr">
         <is>
           <t># 讲座概况
-本次专项讨论会由主讲人（原文未提及姓名）讲解苏阿战争（1979—1989年苏联入侵阿富汗战争）的背景、经过与结果，形式为专题讲解加听众提问。讲座面向对冷战史与地缘政治感兴趣的听众，旨在说明阿富汗的战略地位与“帝国坟场”成因。内容围绕四个板块展开：阿富汗地理与历史背景、苏联出兵经过、各方援助与游击战、苏联撤军原因。核心判断有三：其一，阿富汗地处亚洲中间走廊，谁控制阿富汗谁就控制亚洲咽喉；其二，其国土90%为高原山地、乡村由部落长老制控制，使外部力量难以有效统治；其三，苏联出兵阿富汗属战略性失误，最终被人民战争消耗至撤军。关键锚点包括1979年12月24日平安夜苏联突袭喀布尔、1989年苏联撤军、美国援助“毒刺”防空导弹压制苏军武装直升机。对听众而言，本讲有助于理解冷战格局下大国干预的代价及阿富汗问题的历史根源。
+本次讲座由主讲人（姓名未提及）围绕1979年至1989年苏联入侵阿富汗战争（史称苏阿战争）展开讲解，以专项讨论会形式进行，面向对阿富汗历史与地缘政治感兴趣的听众。讲座覆盖战争背景与起因、阿富汗抵抗与苏联撤军、阿富汗战略地位与帝国坟场成因、圣战者含义与各方援助等板块。核心判断包括：阿富汗地处亚洲中部、被称为亚洲的中间走廊地带，战略地位重要；其国土90%为高原山地，易守难攻，历史上多次被称为帝国坟场；苏联因国王阿明过度导向美国而决定武力介入，1979年12月24日平安夜以兵变政变形式派兵突入阿富汗，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台。讲座以阿富汗地理位置、地形特征及冷战背景为锚点，帮助听众理解苏联出兵动因、阿富汗抵抗力量构成及多国援助格局，对认识阿富汗历史与地缘政治具有参考意义。
 # 核心观点与论证
-## 阿富汗是亚洲咽喉与帝国坟场
-- **地理位置**：阿富汗东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，是兵家必争之地。
-- **地形特征**：国土90%为高原山地地带，易守难攻，是天然的游击战地区，历史上多次获得帝国坟场称号。
-- **控制意义**：谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-- **资源状况**：阿富汗是贫油国，但周边国家如西边的伊朗、北边的土库曼斯坦和塔吉克斯坦都是富油国。
-## 苏联出兵阿富汗的背景与经过
-- **战前态势**：20世纪50年代，阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，国内精英阶层奉行亲英与亲苏两头政策，文化上师从英国，国家建设和工业方面向苏联看齐。
-- **阿明转向**：基辛格评价阿明是用的苏联的火柴点美国的香烟，阿明对苏联日益干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前武力介入。
-- **入侵过程**：1979年12月24日平安夜，苏联以阿富汗请求救援的说法，从东部、中部及西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一个晚上控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台。
-- **国际反应**：众多阿拉伯国家、中国和西方盟国共同不满抵触，合力援助阿富汗，由阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源，支持阿富汗抵抗组织进行长达十年的游击战争。
-## 苏联出兵是战略性失误
-- **勃列日涅夫逻辑**：阿富汗被苏联化为苏联大家庭中的一员，根据勃列日涅夫逻辑不允许任何成员外出，类似之前出兵捷克，阿富汗是必须要下场的。
-- **冷战背景**：同时期处于苏攻美守时期，苏联咄咄逼人进行意识形态扩张及军事霸权恐吓，共同导致苏联出兵阿富汗。
-- **战略错判**：阿富汗是非常特殊的战略要地，加上苏联的错判，导致苏联大大的战略性失误。
-## 阿富汗难以被外部力量控制
-- **部落结构**：除喀布尔和坎大哈等主要城市外，90%地区为乡村部落长老制，政府没有任何控制力，各村落与部落各自为政，任何列强及城市政府无法对高原山地形成有力控制。
-- **中国援助**：中国帮助阿富汗圣战抵抗者，教授抗战时期的地道战、地雷战等战法，与苏联持续进行游击战争。
-- **美国援助**：美国援助了先进的单兵武器毒刺防空导弹（类似火箭筒），可有效压制苏联最先进的雌鹿武装直升机。
-- **苏军困境**：坦克和步兵战车在阿富汗无法形成有效战斗力，因这些装备主要用于平原地带，高原山地需步兵加武装直升机才能有效作战；苏联军事实力看似庞大但武器发挥不了作用，基层官兵普遍厌战，士气一落千丈，最终1989年撤军。
-## 圣战者的作战思想
-- **思想特征**：圣战者具备狂烈激进的伊斯兰圣战思想，以及从上到下宗教式洗脑，导致其像二战时期日本军国主义荼毒下的日本军民一样，抱着同归于尽的思想进行圣战。
-## 中国对阿富汗的援助方式
-- **武器援助**：中国提供了与AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助形式将已饱和的军工业产业稀释掉。
-- **合作默契**：中国与西方盟国为抵抗苏联霸权主义达成秘而不宣的默契。
-- **人员派遣**：中国只提供军火和兵法指导，派专家教授地道战、地雷战，但未派人参战。
+## 阿富汗战略地位与帝国坟场成因
+- **地理位置关键**：阿富汗东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，谁控制了阿富汗谁就控制住亚洲的咽喉。
+- **地形易守难攻**：国土90%为高原山地地带，是天然游击战地区；除喀布尔和坎大哈等主要城市外，大部分地区由部落长老制控制，政府无控制力，列强难以有效统治。
+- **周边富油国环绕**：阿富汗本身是贫油国，但西边伊朗、北边土库曼斯坦和塔吉克斯坦都是富油国，地缘资源价值突出。
+- **历史帝国坟场**：第一次大英帝国入侵后被阿富汗反推回巴基斯坦地区，阿富汗多次获得帝国坟场称号。
+## 苏联出兵阿富汗的起因
+- **阿明两面政策**：20世纪50年代阿富汗同时与苏联及西方保持友好，实行君主立宪制；基辛格评价国王阿明“用苏联的火柴点美国的香烟”，两边要好处。
+- **倒向美国引发苏联不满**：阿明对苏联干涉内政不满、过度导向美国，苏联领导层大为火光；若阿富汗脱离掌控倒向美国，对苏联中亚地区将非常被动。
+- **1979年12月24日平安夜**：苏联以兵变政变形式、借口阿富汗请求救援，从东部、中部、西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台。
+- **冷战背景**：发言人3指出按勃列日涅夫逻辑，不允许苏联成员外出，类似出兵捷克；同时期处于苏攻美守阶段，苏联咄咄逼人进行意识形态扩张与军事霸权恐吓。
+## 阿富汗抵抗与苏联撤军
+- **多国合力援助**：苏联入侵招致众多阿拉伯国家、中国和西方盟国不满，阿富汗和穆斯林国家出动兵源，中国和西方盟国提供武器与情报资源，共同支持抵抗组织。
+- **十年游击战争**：苏联与阿富汗抵抗组织进行长达十年的游击战争，最终扛不住阿富汗人民战争的消耗，于1989年从阿富汗撤出。
+- **中国援助方式**：中国援助了五六式冲锋枪和五六式半自动步枪，通过援助形式稀释已饱和的军工业；只提供军火不派人，但派专家教授地道战、地雷战等抗战时期战法。
+- **美国武器压制**：美国援助毒刺导弹（类似防空导弹的火箭筒），有效压制苏联当时最先进的雌鹿武装直升机；坦克和步兵战车在高原山地无法形成有效战斗力。
+- **苏军士气低落**：苏联基层官兵普遍厌战，不明白为何来此战斗，士气一落千丈，军事实力看似庞大但武器发挥不了作用。
+## 圣战者含义
+- **宗教狂热思想**：圣战者指狂烈的激进的伊斯兰圣战思想，从上到下宗教式洗脑，具备像二战日本军国主义荼毒下的军民一样同归于尽的思想。
 # 金句总结
-&gt; 谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-- 回答听众关于阿富汗为何被多国争夺的提问，点明其地理位置的关键性。
-&gt; 阿富汗多次获得其帝国坟场的称号。
-- 讲述阿富汗历史时，概括列强入侵屡遭失败的结局。
-&gt; 基辛格评价阿富汗当时的国王阿明，说是用的苏联的火柴在点的美国的香烟。
-- 描述阿富汗在美苏之间两头要好处、左右逢源的处境。
-&gt; 苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。
-- 分析苏联重装部队在阿富汗高原山地无法有效作战、最终撤军的原因。
-&gt; 苏军的士气也是一落千丈。
-- 说明苏联基层官兵普遍厌战、不明白为何而战，导致战斗力与士气崩溃。
-&gt; 咱们国家当时也是帮助那个阿富汗圣战抵抗者，教他们兵法，就比如说咱们以前抗战时期所用的，比如地道战、地雷战这样的一个战法。
-- 介绍中国对阿富汗抵抗组织的援助方式，即提供兵法指导而未直接派兵。
+&gt; “谁控制了阿富汗，谁就控制住了亚洲的咽喉。”
+- 背景：回答听众关于阿富汗为何被多国争夺的提问，点明其地理位置的关键性。
+&gt; “他是用的苏联的火柴在点的美国的香烟。”
+- 背景：引用基辛格对阿富汗国王阿明的评价，说明其同时向苏联和西方两边要好处的墙头草立场。
+&gt; “这个国家百分之九十都是处于高原山地地带，就是一个天然的游击战地区。”
+- 背景：解释阿富汗帝国坟场称号的成因，指出其地形易守难攻、列强难以有效控制。
+&gt; “苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。”
+- 背景：论证苏联在阿富汗陷入困境的原因，其重装部队在高原山地无法形成有效战斗力。
+&gt; “苏军的士气也是一落千丈。”
+- 背景：说明苏联基层官兵普遍厌战，不明白为何来阿富汗作战，最终导致撤军。
 # Q&amp;A 环节
-**听众**：阿富汗到底有啥好呀？为啥都想打它？
-**主讲人**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-**听众**：是不是阿富汗有石油啊？
-**主讲人**：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
-**听众**：其实这个我感觉得用当时的冷战思维来看，因为阿富汗当时被苏联化为苏联势力、苏联大家庭中的一员。根据勃列日涅夫的逻辑，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，加上苏联这个错判，导致苏联大大的战略性失误。
-**主讲人**：对的，同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人地进行意识形态的扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
-**听众**：之前看那个阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
-**主讲人**：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民那样，不顾一切地抱着同归于尽的思想进行圣战。
-**听众**：其实这次苏阿战争之前，已经有三次英阿战争，阿富汗被称为帝国坟场，可以简单说一下为什么这个位置这么难打？虽然它的国土面积没有那么大，经济实力又没有那么好。
-**主讲人**：因为这个国家百分之九十都是处于高原山地地带，是一个天然的游击战地区。除了喀布尔和坎大哈那几个主要城市以外，剩下大部分百分之九十的地区都是乡村部落长老制，政府没有任何控制力，由部落长老控制，各个村落与部落各自为政，导致任何列强以及阿富汗的城市政府都无法对广大的高原山地形成有力控制。同时期咱们国家帮助阿富汗圣战抵抗者，教他们抗战时期所用的地道战、地雷战等战法，和苏联持续进行游击战争；美国也援助了比较先进的单兵武器，比如毒刺防空导弹，可以有效压制苏联最先进的武装直升机雌鹿。坦克和步兵战车在阿富汗无法形成有效战斗力，因为这些装备主要用于平原地带，在高原山地还是要以步兵加武装直升机才能形成有效战斗力。苏联军事实力看似庞大，但武器发挥不了作用，基层官兵普遍厌战，士气一落千丈，最终1989年扛不住压力撤军。
-**听众**：咱们男生基本都说完了，都说过一遍了。
-**主讲人**：也是给了一些枪炮，比如咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助的形式把咱们国家已经饱和的军工业产业稀释掉，同时大家为了抵抗苏联霸权主义和西方盟国达成了一种秘而不宣的默契。
-**听众**：只提供军火，但是没有派人。
-**主讲人**：专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
+**发言人2**：阿富汗到底有啥好呀？为啥都想打它？
+**发言人1**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+**发言人2**：是不是阿富汗有石油啊？
+**发言人1**：它这个国家相对来说是个贫油国，但周边国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
+**发言人3**：其实这个我感觉得用当时的冷战思维来看，阿富汗当时被苏联化为苏联大家庭中的一员。根据勃列日涅夫的逻辑，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，加上苏联这个错判，导致苏联大大的战略性失误。
+**发言人1**：对的，同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人地进行意识形态的扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
+**发言人3**：之前看阿富汗那边把部队叫什么圣战者，这个是什么意思？
+**发言人1**：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民一样，不顾一切地抱着同归于尽的思想进行圣战。
+**发言人3**：其实这次苏阿战争之前，已经有三次英阿战争，阿富汗被称为帝国坟场，可以简单说一下为什么这个位置这么难打？
+**发言人1**：因为这个国家百分之九十都是高原山地地带，是天然的游击战地区。除了喀布尔和坎大哈那几个主要城市以外，剩下大部分地区都是乡村部落长老制，政府没有任何控制力，各个村落与部落各自为政，导致任何列强以及阿富汗城市政府都无法对广大高原山地地区形成有力控制。同时期咱们国家帮助阿富汗圣战抵抗者，教他们地道战、地雷战等抗战时期的战法；美国也援助了比较先进的单兵武器，比如毒刺防空导弹，可以有效压制苏联最先进的雌鹿武装直升机。坦克和步兵战车在阿富汗没法形成有效战斗力，因为这些装备主要用于平原地带，高原山地还是要以步兵加武装直升机才能形成有效战斗力。苏联军事实力看似庞大，但武器发挥不了任何作用，基层官兵普遍厌战，士气一落千丈，最终1989年从上到下扛不住压力撤军。
+**发言人2**：咱们男生基本都说完了，都说过一遍了。
+**发言人1**：也是给了一些枪炮，比如咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助形式把咱们国家已经饱和的军工业产业稀释掉，同时大家为了抵抗苏联霸权主义和西方盟国达成了一种秘而不宣的默契。
+**发言人3**：只提供军火，但是没有派人。
+**发言人1**：专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
@@ -17033,7 +17086,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3129/3290</t>
+          <t>3129/2896</t>
         </is>
       </c>
     </row>
@@ -17226,64 +17279,59 @@
       <c r="C53" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由4位发言人（发言人1、发言人2、发言人3、发言人4）围绕各国文学特点展开漫谈式分享，由《白夜行》的悬疑叙事与阴暗结局切入，借《菊与刀》引出对日本民族性格的观察，随后依次比较法国、英国、俄国、美国文学在底层描写、抗争精神与理想主义上的差异，并延伸至中国底层文学的政策限制、台湾电影《假如我是真的》与上山下乡历史背景、苏联时期作家作品，最后以《西游记》狮驼岭章节的黑暗解读收束。讨论以分享观点为主，未形成统一结论，整体按议题逐块推进，从日本文学出发，经多国文学比较，再转入历史社会背景与具体作品解读，发言间相互补充与引申。
+本次讨论为多人闲聊式文学漫谈，由发言人2主导引导，发言人1、3、4参与，围绕各国文学特点展开比较。讨论从东野圭吾《白夜行》的悬疑叙事切入，引出日本文学与《菊与刀》所描绘的民族性格，随后依次比较法国、英国、俄国、美国文学对底层民众的描写与批判性，并延伸至国内底层文学受限、台湾电影《假如我是真的》改编背景，以及《西游记》狮驼岭章节的宗教批判。整体以分享观点为主，未形成统一结论，讨论按议题逐块推进，从日本文学过渡至各国文学比较，再聚焦《西游记》具体章节，发言较为发散。关键锚点包括《白夜行》《菊与刀》《悲惨世界》《古拉格群岛》及狮驼岭距灵山约500公里等。
 # 发言要点
 ## 日本文学《白夜行》讨论
-- **发言人1**：《白夜行》是悬疑小说，叙事手法独特，上来都是隐藏信息，让人一直猜不到真相，每个人都有嫌疑，但结局非常阴暗。
-- **发言人2**：美国作家本尼迪克特《菊与刀》生动描绘了日本人性格特点，《白夜行》也能体现这一点，并由此引出各国文学偏好话题。
+- **发言人1**：《白夜行》是悬疑小说，叙事手法新颖，上来都是隐藏线索，让人一直猜不到真相，每个人都有嫌疑，但结局非常阴暗。
+- **发言人2**：美国作家本尼迪克特《菊与刀》生动描绘日本人性格特点，《白夜行》也能体现这一点，由此引出各国文学比较。
 ## 各国文学特点比较
-- **发言人2**：法国文学体现浪漫的理想主义精神和奉献，尤其在《悲惨世界》中生动体现。
-- **发言人4**：法国相对英国小说，描绘底层民众更多一些，英国的多是贵族生活。
-- **发言人1**：法国挺爱革命，有抗争精神；英国想维持他们那套，法国确实革命了好多。
-- **发言人2**：英国后期土地承载不了人口膨胀，以英国、爱尔兰为主带头移民北美新大陆，这是根本原因。
-- **发言人1**：英国像《圣诞欢歌》《雾都孤儿》也讲底层，写贵族和穷人之间有鸿沟，穷人把希望寄托在宗教或虚无的东西上。
-- **发言人2**：美国历史短，叙事风格不同于欧洲，更多表现在现代社会，与欧洲理想主义的精神图腾不太一样。
-- **发言人1**：美国历史太少，美洲大陆没发生欧亚大陆那么多悲惨事情，相对还是幸福的，如《了不起的盖茨比》。
-- **发言人2**：北美大平原农业资源广阔，美国今天经济不好也永远不缺粮食；欧亚大陆的瘟疫、大饥荒在美国从未发生过，美国人无法真正理解饥荒为何物。
-- **发言人1**：电影《一九四二》讲的就是大饥荒和战乱。
-- **发言人2**：日本人能打垮国民党军队，是因为给灾民发放粮食，而国民党对灾区视而不见，结果日本人占领了河南省大部地区。
-- **发言人1**：有人打仗给日本人报情报换取粮食，这是人性，没办法。
-## 中国底层文学与历史背景
-- **发言人1**：国内写底层的其实写得很深刻，像《平凡的世界》，但好多因政策原因不让看了，以前很多根据底层小说改编的电影也不让看。
-- **发言人2**：台湾电影《假如我是真的》改编自俄国果戈里《钦差大臣》，结合文革知青上山下乡真实事件，上世纪七十年代末、八十年代初拍摄。
-- **发言人2**：当时台湾和大陆搞舆论宣传战、意识形态攻略，台湾把大陆上山下乡、文革时期的不公通过电影批判出来。
-- **发言人1**：他们批判自己，也批判平衡，台湾总会拍电影。
-## 俄国文学与苏联时期作品
-- **发言人2**：个人比较喜欢契诃夫，如《变色龙》《装在套子里的人》《凡卡》。
-- **发言人2**：苏联时期喜欢格罗斯曼，他是红军战地记者，写了《命运与生活》，以小说方式出版红军后期进入欧洲后看似不公的问题，从平民视角看苏联红军的基层真实形象。
-- **发言人2**：《古拉格群岛》真正把人性黑暗面批判出来，最早出版版本是法语版，俄语版要等苏联解体后才发行。
-- **发言人2**：俄国文豪如列夫·托尔斯泰是前线俄军，把老百姓疾苦、不公与贵族奢华对比讽刺；因沙俄新闻管制严厉，以小说方式发表。
-- **发言人2**：俄国文学与法国文学有相似也有不同，对人性丑恶的揭露与批判更为讽刺，《古拉格群岛》和契诃夫作品都是表现。
-- **发言人2**：高尔基《海燕》是老百姓被压迫久了之后的呐喊和挣扎，是走投无路后奋起的反抗。
-- **发言人1**：苏联时期作者挺多，但看得很少，反倒是高尔基因为正面宣传看得比较多。
-- **发言人1**：初中高中时有英语读物要求中英对照读名著，自己不看英语只看汉语，觉得挺有意思。
-## 《西游记》狮驼岭章节解读
-- **发言人2**：狮驼岭章节生动揭露佛教世界的虚伪，佛门三大圣兽青狮、白象和大鹏偷下界，把城池所有人吃掉，扶植小妖成为国家公民。
-- **发言人2**：唐僧师徒路过时满国尸骸遍地，孙悟空都不战而弃、发抖；原著描写人皮当地毯、骷髅头骨当装饰物和器具，此地距离灵山不过500公里左右。
-- **发言人2**：这与佛门所说普度众生、众生平等大相径庭；旧社会西藏王公大臣就是这种状态，共产党没解放西藏悲剧会延续到今天。
-- **发言人2**：吴承恩在古代就预测并批判揭露佛教在部分地区是上层王公大臣迷惑底层民众、高压奴役的统治工具，这是汉传佛教和藏传佛教截然不同的本质。
-- **发言人4**：问狮驼岭是啥，这个是不是没有拍到电视剧。
-- **发言人2**：有拍，但没把那些惨案讲得那么生动，最后佛祖出手收回，孙悟空终究要被大鹏精打败，大鹏精是全书唯一能遛猴子的反派。
-- **发言人1**：电视剧就拍几个妖精是大王，过去全给干了；黑神话悟空也没设计那一章，太血腥不好过审，而且意义深刻，剧情既要委婉又要深刻很难。
+- **发言人2**：法国文学体现浪漫的理想主义精神和奉献，如《悲惨世界》；雨果作品非常世界。
+- **发言人4**：法国小说比英国小说更多描绘底层民众，英国的多写贵族生活。
+- **发言人1**：法国爱革命，有抗争精神；英国想维持贵族秩序，法国确实革命了很多次。
+- **发言人2**：俄国文学更讽刺人性丑恶，如契诃夫《变色龙》《装在套子里的人》《凡卡》；《古拉格群岛》真正批判人性黑暗面，最早出版法语版，俄语版要等苏联解体后才发行。
+- **发言人4**：俄国文学比法国文学更多曲折，戏剧性更明显。
+- **发言人1**：国内《平凡的世界》等底层小说写得深刻，但因政策原因很多不让看，相关电影也受限。
+- **发言人2**：台湾电影《假如我是真的》改编自俄国果戈里《钦差大臣》，结合文革知青上山下乡真实事件，上世纪七十年代末、八十年代初拍摄，是当时台湾与大陆舆论宣传战、意识形态攻势的一部分。
+- **发言人2**：苏联作家格罗斯曼是红军战地记者，写《命运与生活》，从平民视角描写红军后期进入欧洲后看似不公的问题。
+- **发言人1**：英国《圣诞欢歌》《雾都孤儿》也讲底层人，描写贵族与穷人之间的鸿沟，穷人把希望寄托在宗教或虚无的东西上。
+- **发言人2**：欧洲土地无法承载人口膨胀，以英国、爱尔兰为主带头移民北美新大陆，这是根本原因。
+- **发言人2**：美国文学历史较短，叙事风格不同于欧洲，更多表现在现代社会，与欧洲理想主义精神图腾差别较大。
+- **发言人1**：美国历史太短，美洲大陆没发生欧亚大陆那么多悲惨事件，相对幸福；看过《了不起的盖茨比》。
+- **发言人2**：北美大平原农业资源广阔，美国经济不好也永远不缺粮食；黑死病、天花、饥荒、旱灾、蝗灾在美国从未发生过，美国人无法真正理解饥荒为何物。
+- **发言人1**：电影《一九四二》讲大饥荒和战乱。
+- **发言人2**：日本人给灾民发放粮食，国民党对灾区视而不见，导致日本人占领河南省大部地区。
+- **发言人1**：有人为换取粮食给日军送情报，这是人性，没办法。
+- **发言人2**：列夫·托尔斯泰是前线俄军，把百姓疾苦与贵族奢华对比讽刺，因沙俄新闻管制严厉而以小说方式发表；俄国文学比法国更讽刺人性丑恶。
+- **发言人1**：初中高中时读中英对照英语读物，光看汉语部分就觉得名著很有意思。
+- **发言人2**：高尔基《海燕》是老百姓被压迫久了之后的呐喊和反抗，高尔基感觉特别正面。
+- **发言人1**：高尔基偏诗歌形式写底层人。
+## 《西游记》狮驼岭章节讨论
+- **发言人2**：《西游记》以小说形式揭露佛教世界的虚伪，狮驼岭章节尤为明显——佛门三大圣兽青狮、白象、大鹏偷离佛门到下界作妖，吃光城池所有人，扶植小妖成为国家公民，孙悟空都不战而弃、浑身发抖。
+- **发言人2**：狮驼岭原著描写人皮当地毯、骷髅头骨当装饰物和器具，此地距离灵山不过500公里左右，却发生如此人伦惨剧，与佛门普度众生、众生平等理念大相径庭。
+- **发言人2**：吴承恩在古代就已预测并批判佛教被上层王公大臣用来迷惑、高压奴役底层民众，而非真正宣传众生平等；并联系旧社会西藏、印度菩提迦耶附近类似惨剧，认为共产党解放西藏终结了这种悲剧。
+- **发言人4**：问狮驼岭章节是否没拍到电视剧。
+- **发言人2**：有拍，但没把那些惨烈细节讲得那么生动。
+- **发言人1**：电视剧只拍几个妖精被孙悟空全干掉了，没表现那些内容；《黑神话悟空》也没设计狮驼岭那一章，太血腥、不太好过审，而且意义深刻，剧情既要委婉又要深刻，很难设计。
+- **发言人2**：狮驼岭章节里如果不是佛祖出手，孙悟空终究要被大鹏精打败；大鹏精是《西游记》全剧中唯一能遛猴子的反派角色。
 # 共识形成
-- **一致意见**：与会者普遍认同《白夜行》叙事手法独特、结局阴暗，并认可《菊与刀》对日本人性格特点的描绘；在各国文学比较中，**法国文学体现抗争精神与浪漫理想主义（如《悲惨世界》）**、英国文学多描写贵族生活、俄国文学对底层民众的描绘更生动且对人性丑恶的揭露与批判更为讽刺（如契诃夫、托尔斯泰、《古拉格群岛》）、美国文学历史短且多表现现代社会，这些判断得到多人呼应。
-- **倾向性认识**：发言人1与发言人4认为法国文学比英国文学更侧重描绘底层民众，英国文学多写贵族生活；发言人2补充法国文学具有浪漫理想主义精神与奉献色彩。发言人2认为俄国文学在底层描写上比法国更生动，发言人4回应俄国文学戏剧性更明显、更曲折。
-- **主要分歧点**：在底层文学受限问题上，发言人1主张国内底层文学（如《平凡的世界》）因政策原因受限，发言人2则以台湾电影《假如我是真的》为例，指出其结合俄国《钦差大臣》与文革知青上山下乡事件，是台湾对大陆舆论宣传战的产物——两人对国内底层文学受限原因的判断口径不一致（政策限制 vs 两岸舆论对抗背景）。在《西游记》狮驼岭解读上，发言人2认为该章节批判佛教被上层利用、汉传与藏传佛教本质不同，发言人1与发言人4未直接反驳，但仅就电视剧与游戏未充分展现该章节黑暗内容（人皮地毯、骷髅装饰等）表示认同，未对发言人2的宗教批判结论表态。
+- **一致意见**：与会者普遍认同各国文学对底层民众的描写存在显著差异，且文学常以批判性反映社会现实。发言人2、发言人1、发言人4均认可法国文学体现抗争精神与浪漫理想主义（如《悲惨世界》），俄国文学更侧重对人性丑恶的揭露与讽刺（如契诃夫、托尔斯泰及《古拉格群岛》），英国文学如《圣诞欢歌》《雾都孤儿》亦涉及底层描写。
+- **倾向性认识**：发言人2提出美国文学历史较短、侧重现代社会，与欧洲理想主义风格不同；发言人1补充国内《平凡的世界》等底层小说因政策原因受限，发言人2进一步指出台湾电影《假如我是真的》改编自俄国《钦差大臣》并结合知青上山下乡事件，用于两岸舆论宣传战。
+- **主要分歧点**：发言人4认为法国小说比英国小说更多描绘底层民众，英国多写贵族生活；发言人1则认为英国文学（如狄更斯作品）同样大量描写底层，双方对英法文学底层描写的侧重程度认识不一致。此外，发言人2认为《西游记》狮驼岭章节揭露佛教虚伪，并联系西藏历史，发言人1、4未明确反对，但发言人1仅表示该章节「挺吓人」，未对宗教批判观点表态。
 # 待探讨问题与后续
-- **未确认**：发言人1提到国内底层文学（如《平凡的世界》）「因政策原因不让你看了」，但未说明具体政策依据或哪些作品受限，此说法仅为个人观点，未获其他成员证实或展开。
-- **待核实**：发言人2称《古拉格群岛》「最早出版的版本还是法语版的，俄语版的还要等到苏联解体之后才发行」，此版本时间线未在讨论中进一步核实。
-- **未确认**：发言人2称台湾电影《假如我是真的》「改编自俄国小说《钦差大臣》并结合文革知青上山下乡事件」，发言人3当场追问「他讲的是啥呀」，发言人2以「先不剧透」回避，影片具体情节与改编关系未展开说明。
-- **未定论**：发言人2认为《西游记》狮驼岭章节中吴承恩批判佛教被上层利用、汉传佛教与藏传佛教「本质截然不同」，此解读为发言人2个人观点，其他成员未表示认同或反对，也未就此达成一致。
-- **未确认**：发言人2称狮驼岭章节「此地距离灵山也不过500公里左右」，并以此类比西藏与菩提迦耶的距离，该地理数据未在讨论中核实。
-- **未定论**：发言人1提到《黑神话：悟空》未设计狮驼岭章节，推测「不太好过审」「太血腥」，但未确认游戏方是否确有相关设计或删减安排，仅为猜测。</t>
+- **未确认**：发言人1提到国内《平凡的世界》等底层小说及改编电影「因政策原因不让看」，但未具体说明是哪些作品、何种政策限制，也未展开讨论。
+- **未确认**：发言人2称《古拉格群岛》最早出版版本为法语版、俄语版要等苏联解体后才发行，此说法未获其他成员验证或补充。
+- **待核实**：发言人2称台湾电影《假如我是真的》改编自俄国小说《钦差大臣》并结合文革知青上山下乡事件，发言人3追问「讲的是啥呀」，发言人2以「不剧透」带过，影片具体情节与改编细节未展开。
+- **未定论**：发言人2认为《西游记》狮驼岭章节批判佛教虚伪，并联系西藏历史、藏传佛教与汉传佛教本质差异，发言人1仅回应「确实挺吓人」，未就此观点表态或反驳，该解读是否成立未形成讨论结论。
+- **未定论**：发言人1提到《黑神话悟空》未设计狮驼岭章节，推测因「太血腥、不太好过审、意义深刻难设计」，但未确认游戏开发方是否确有相关考虑。
+- **未确认**：发言人2称大鹏精是《西游记》全剧中唯一能「遛猴子」的反派角色，此判断未获其他成员回应或验证。</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5886/3302</t>
+          <t>5886/2961</t>
         </is>
       </c>
     </row>
@@ -17356,82 +17404,78 @@
       <c r="C54" t="inlineStr">
         <is>
           <t># 全文摘要
-本次例会由产品经理主持，产品、开发1、开发2参与，围绕手机图库项目进展，对齐了智能分类与相册推荐改版、AI智能标签接口、同步模块、缩略图渲染、时间轴加载优化、AI修图预留及里程碑计划等议题。产品侧汇报高保真原型V1.5版已出，用户调研反馈隐私相册入口太深，产品经理同意将入口提升至首部顶部二级菜单并要求出交互方案评审。开发侧同步多项技术进展：AI标签V2模型准确率提升约88%，但单次请求耗时从800毫秒增至约1.5秒，决定采用本地缓存策略并采纳端侧预过滤方案；同步模块因队列积压超1000张导致部分机型OOM崩溃，维持分片加载方案；缩略图渲染改用新解码库，内存占用降约30%，主流机型帧率稳定60帧；时间轴采用本地索引预加载方案。AI修图本次不实现，预留接口和插件化架构。里程碑按原定计划月底封版，内测包暂定下周三发。
+本次例会由产品经理主持，产品、开发1、开发2三方参与，围绕手机图库项目进展对齐排期与风险。会议覆盖智能分类与相册推荐改版、AI智能标签接口、同步模块与内存管理、缩略图渲染、时间轴加载优化、AI修图功能预留及项目里程碑等议题。关键结论包括：隐私相册入口提升至首部顶部二级菜单；AI标签接口采用本地缓存加端侧预过滤方案；同步模块按分片加载推进；批量删除锁死Bug临时规避、正式修复排进V1.2；时间轴加本地索引预加载；AI修图预留接口并做插件化架构。关键数字锚点：AI识别模型准确率提升约88%、单次请求耗时从800毫秒涨至约1.5秒、内存占用降约30%、月底封版、下周三发内测包。
 # 分段速览
-## 00:00:00-00:01:23 开场与产品侧进展
-产品经理开场说明会议目的：过手机图库项目整体进展，对齐排期与潜在风险，按产品侧、开发侧、总结的顺序进行。产品侧汇报近两周重点推进智能分类和相册推荐改版，高保真原型已出V1.5版，调整了网格视图交互逻辑和长按微动效反馈。测试反馈低端机上滑列表偶尔掉帧，已与开发2沟通，拟通过降低预览图缩放级别换取帧率。用户调研收到不少关于隐私相册入口太深的吐槽，建议下一版将入口提到首部顶部二级菜单。产品经理回应：隐私相册入口提升不算大改动，同意推进并要求出交互方案评审；掉帧问题需抓紧，下周将进入性能压测。
+## 00:00:00-00:01:23 会议开场与产品侧进展
+产品经理（发言人1）开场说明会议目的：过手机图库项目整体进展，对齐排期与潜在风险，按产品侧、开发侧、总结的顺序进行。产品（发言人2）同步智能分类和相册推荐改版进展：高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈；低端机上滑列表偶发掉帧，已与开发2沟通考虑降低预览图缩放级别；用户调研反馈隐私相册入口太深，建议下一版提升至首部顶部二级菜单。产品经理回应：隐私相册入口调整不算大改动，要求产品出交互方案供评审；掉帧问题需抓紧，下周将进入性能压测。
 ## 00:01:51-00:03:19 AI标签接口与同步模块问题
-开发1汇报AI智能标签接口进展：V2版识别模型已跑通，准确率较上一代提升约88%，但因新增视频帧提取功能，单次请求耗时从800毫秒涨至约1.5秒，需产品侧评估用户接受度，备选方案是改异步推送。产品反对异步推送，认为用户点开相册无实时结果会感觉功能卡死，提出先做本地缓存策略——首次识别慢、之后本地读库秒出。开发1确认可行，计划下午拉分支改逻辑，预计三天联调完，但提示缓存命中率低时仍需回溯。开发1同时提出云相册同步模块断点续传在弱网环境下出现状态机紊乱。开发2反馈同步队列积压超1000张时部分机型出现OOM崩溃，iOS尤其严重，已采用分片加载机制每次拉50张，但会拖慢同步进度，需与产品商量是否加后台静默同步权限或允许用户手动设置同步频率。
+开发1（发言人3）汇报AI智能标签接口：V2识别模型已跑通，准确率提升约88%，但新增视频帧提取功能导致单次请求耗时从800毫秒涨至约1.5秒，提出是否改异步推送。产品（发言人2）否决异步推送，建议先做本地缓存策略——首次识别慢、之后本地读库秒出，开发1确认可行，预计三天联调完，但提示缓存命中率低时需回溯。开发1同时反馈云相册同步模块断点续传在弱网环境下出现状态机紊乱。开发2（发言人4）确认同步队列积压超1000张时部分机型出现OOM崩溃，尤其iOS内存回收激进，已采用分片加载机制每次拉50张，但拖慢同步进度，提出加后台静默同步权限或允许用户手动设置同步频率。
 ## 00:03:57-00:05:03 同步方案与缩略图渲染优化
-产品经理指出后台同步权限审核严、大概率下不了，决定维持分片加载方案但进度不能拖。开发2汇报缩略图渲染优化：改用新图片解码库，将JPEG硬解换为软解，内存占用降约30%但CPU占用上升；已在主流三款机型灰度，帧率稳定60帧、低端机约50帧，周四性能报告今晚可出初稿。另提出批量删除照片时若同时触发回收站重建索引，数据库偶尔锁死，已用消息队列排队处理作临时规避，正式修复预计排到下下周版本。产品经理决定临时规避先稳住，正式修复排进V1.2迭代。
-## 00:05:35-00:07:25 端侧预过滤与时间轴加载优化
-产品经理提出端侧预过滤思路：先用轻量级模型扫一遍，过滤明显非图片的gif或截图，剩余再走全量云端识别，预计可将平均耗时压下一半。开发1认可该思路，将评估模型体积和端侧推理开销，若放端侧跑需再申请200兆本地缓存空间，请产品评估对安装包体积的影响。产品回应安装包加两三百兆问题不大，建议做成按需加载——用户首次进图库智能标签时才触发下载，平时不占空间，开发1确认可用现有资源下发模块实现，约两天搞定，并拉开发2配合端侧推理联调。开发1另提出时间轴视图加载问题：测试提了三个优高优Bug，滑动到二十年前老照片时页面卡死三秒以上，原因是历史图片EXIF解析耗时加磁盘IO瓶颈，准备加本地索引预加载，最近三个月照片建树状结构、滑到底部动态加载旧数据。产品经理同意改动，但提醒注意别与云同步模块抢资源。开发2确认不会冲突——预加载放主线程IO池、同步放子线程后台服务，但预加载需用户授权媒体和存储权限，若首次拒绝需引导弹窗，弹窗交互由产品设计。
-## 00:07:48-00:09:42 AI修图预留与管线重构
-产品提出运营希望下版本加AI修图快捷入口（一键去背景、智能调色），本次排期可能塞不进去，想提前占坑、架构上留好接口。产品经理决定本次主线是性能和分类，不硬塞AI修图，在PRD里先写好接口逻辑和UI占位，开发侧把模块抽象成插件化架构，下次迭代直接接入；后端接口按标准RESTful加Swagger文档输出。开发1确认微服务架构下按规范出文档很轻松，同时指出端侧若预留AI修图渲染通道，需重构当前耦合较深的图片处理管线。开发2表示近期也在考虑管线优化——现在每加滤镜就得改底层代码，拟将渲染层抽成插件化、用GLSL写统一接口，工作量约多一周，需产品经理确认能否把非核心Bug修复往后挪。产品经理同意调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化，要求开发2今天下班前评估精确工作量，开发1排联调时间、尽量周五前跑通主干流程。
-## 00:10:19-00:12:18 里程碑与内测安排
-产品确认下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查，同时制作AI修图占位图保持视觉一致性，并询问项目里程碑与内测包时间。产品经理确认里程碑按原定计划月底封版，内测包暂定下周三发，届时拉体验官群重点跑AI分类和同步模块，产品准备反馈收集表、开发准备日志抓取。开发1提出需与数据库组对齐索引策略，产品经理同意拉群让DBA配合优化建表。开发2确认今晚继续跑分片加载和渲染优化压测数据，并询问周四性能评审是否将iOS和安卓对比数据单独列版，产品经理同意分开列、由测试组合并为一份总览。产品经理下午两点参加UI走查，产品承诺十一点半前发稿。会议结束。
+产品经理（发言人1）判断后台同步权限审核严、大概率下不了，决定按分片加载方案走但进度不能拖，并询问缩略图渲染卡顿优化进展。开发2（发言人4）汇报：采用新图片解码库，将JPEG硬解换软解，内存占用降约30%但CPU占用上升；已在主流三款机型灰度，帧率稳定60帧、低端机约50帧；周四性能报告今晚出初稿。另提出批量删除照片时若同时触发回收站重建索引，数据库偶发锁死，已用消息队列临时规避，正式修复排到下下周版本。产品经理决定临时规避先稳住，正式修复排进V1.2迭代。
+## 00:05:03-00:07:01 端侧预过滤与时间轴加载优化
+产品经理（发言人1）建议开发1在端侧做初步筛选：先用轻量级模型过滤gif或截图，剩余走全量云端识别，平均耗时压下一半。开发1（发言人3）认可该思路，需评估模型体积和端侧推理开销，若端侧跑需再申请两百兆本地缓存空间。产品（发言人2）表示安装包加两三百兆问题不大，建议做成按需加载——用户首次进智能标签时才触发下载，开发1确认用现有资源下发模块约两天搞定。开发1另反馈时间轴视图滑动到二十年前老照片时页面卡死三秒以上，测试提了三个优高优Bug，原因是历史图片EXIF解析耗时加磁盘IO瓶颈，计划加本地索引预加载，最近三个月照片建树状结构、滑到底部动态加载旧数据。
+## 00:07:01-00:09:15 预加载资源隔离与AI修图预留
+产品经理（发言人1）同意时间轴预加载方案，但提醒注意别与云同步模块抢资源。开发2（发言人4）确认不会冲突——预加载放主线程IO池、同步放子线程后台服务，但预加载需用户授权媒体和存储权限，若首次拒绝需引导弹窗，交互设计由产品负责。产品（发言人2）表示引导弹窗明天出稿，走柔和提示路线；另同步运营反馈希望下版本加AI修图快捷入口（一键去背景、智能调色），虽本次排不进但想提前占坑。产品经理决定本次主线是性能和分类，不硬塞AI修图，在PRD预留接口逻辑和UI占位，开发侧做成插件化架构。开发1提出后端接口按标准RESTful加Swogger文档输出；开发2建议趁此将图片处理管线重构，渲染层抽成插件化、用GLSL写统一接口，工作量多一周左右。
+## 00:09:42-00:12:18 优先级调整与收尾安排
+产品经理（发言人1）决定调整优先级：非核心UI微调往后排，资源给到管线重构和AI标签优化；要求开发2今天下班前评估精确工作量，开发1排联调时间、周五前跑通主干流程；周四性能压测由测试部配合，需拿达标数据。产品（发言人2）确认下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查，并制作AI修图占位图。项目里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块。开发1提出需与数据库组对齐索引策略，产品经理安排拉群由DBA配合优化建表；开发2确认今晚继续跑压测数据，并询问性能报告是否将iOS和安卓对比数据单独列版，产品经理同意分开列、由测试组合并成一份总览。
 # 要点梳理
 ## 智能分类与相册推荐改版
-- **高保真原型**：已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈
-- **低端机掉帧**：测试反馈上滑列表偶尔掉帧，计划通过降低预览图缩放级别改善，已与开发2沟通
-- **隐私相册入口**：用户调研反馈入口太深，建议下一版提升至首部顶部二级菜单；产品经理同意，不算大改动，要求出交互方案评审
-## AI智能标签接口与性能
-- **模型升级**：V2识别模型已跑通，准确率较上一代提升约88%
-- **耗时问题**：新增视频帧提取功能后，单次请求耗时从800毫秒增至约1.5秒
-- **异步推送方案**：产品明确反对，认为用户点开相册无实时结果会感觉功能卡死
-- **本地缓存策略**：采用首次识别慢、之后本地读库秒出的方案；开发1下午拉分支改逻辑，预计三天联调完；缓存命中率低时仍需回溯
-- **端侧预过滤**：先用轻量级模型过滤gif或截图，再走云端识别，预计平均压一半耗时；需评估模型体积和端侧推理开销，可能申请200兆本地缓存空间
-- **按需加载**：用户首次进智能标签时才触发下载，平时不占空间；用现有资源下发模块即可，预计两天完成
+- **高保真原型**：已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈。
+- **低端机掉帧**：上滑列表偶尔掉帧，已与开发2沟通，考虑通过降低预览图缩放级别换帧。
+- **隐私相册入口**：用户调研反馈入口太深，建议下一版提升至首部顶部二级菜单；产品经理确认不算大改动，由产品出交互方案供评审。
+## AI智能标签接口与性能优化
+- **识别模型**：后端V2版已跑通，准确率较上一代提升约88%。
+- **请求耗时**：因新增视频帧提取功能，单次请求耗时从800毫秒涨至约1.5秒。
+- **异步推送方案**：产品否决，认为用户点开相册无实时结果会感觉功能卡死。
+- **本地缓存策略**：开发1确认可行，加CQLite缓存层，首次识别慢、之后本地读库秒出，预计三天联调完；缓存命中率低时仍会回溯。
+- **端侧预过滤**：产品经理建议先用轻量级模型过滤gif/截图，再走全量云端识别，平均耗时压下一半；开发1评估模型体积和端侧推理开销，需申请约200兆本地缓存空间。
+- **按需下载**：模型按需加载，用户首次进图库智能标签时触发下载，平时不占空间；用现有资源下发模块，约两天搞定。
 ## 同步模块与内存管理
-- **OOM崩溃**：同步队列积压超1000张时部分机型崩溃，iOS内存回收机制激进尤其严重
-- **分片加载**：已实施每次拉50张、处理完再拉下一批的机制，但会拖慢同步进度
-- **后台同步权限**：审核严，大概率无法申请；决定维持分片加载方案，但进度不能拖
-## 缩略图渲染与性能优化
-- **解码库优化**：JPEG硬解换软解，内存占用降约30%，CPU占用上升
-- **灰度测试**：主流三款机型帧率稳定60帧，低端机约50帧；周四性能报告初稿今晚出
-- **数据库锁死Bug**：批量删除照片同时触发回收站重建索引时偶发锁死，已用消息队列排队临时规避；正式修复排进V1.2迭代
+- **OOM崩溃**：同步队列积压超1000张时部分机型崩溃，iOS内存回收机制较激进。
+- **分片加载**：开发2已加机制，每次拉50张处理完再拉下一批；后台静默同步权限审核严、大概率下不了，按分片方案走但进度不能拖。
+## 缩略图渲染与性能评审
+- **解码优化**：JPEG硬解换软解，内存占用降约30%，CPU占用上升。
+- **灰度数据**：主流三款机型帧率稳定60帧，低端机约50帧；周四性能报告初稿今晚出。
+- **数据库锁死Bug**：批量删除照片同时触发回收站重建索引时偶发锁死，已用消息队列临时规避，正式修复排进V1.2迭代。
 ## 时间轴视图加载优化
-- **卡死问题**：滑动到二十年前老照片时页面卡死三秒以上，测试提了三个优高优Bug
-- **根因**：历史图片EXIF解析耗时过长，叠加磁盘IO瓶颈
-- **预加载方案**：最近三个月照片建树状结构，滑到底部动态加载旧数据；需与云同步模块隔离资源
-- **权限引导**：预加载需用户授权媒体和存储权限，拒绝时需引导弹窗；产品明天出稿，走柔和提示路线
+- **卡死问题**：滑动到二十年前老照片时页面卡死三秒以上，测试提了三个优高优Bug；原因为历史图片EXIF解析耗时加磁盘IO瓶颈。
+- **预加载方案**：加本地索引预加载，最近三个月照片建树状结构，滑到底部动态加载旧数据；开发2确认预加载放主线程IO池、同步放子线程后台服务，互不冲突。
+- **权限引导**：预加载需用户授权媒体和存储权限，若首次拒绝需引导弹窗，产品明天出稿、走柔和提示路线。
 ## AI修图功能预留
-- **需求来源**：运营反馈希望下版本加AI修图快捷入口（一键去背景、智能调色）
-- **本次范围**：不硬塞进当前迭代，主线为性能和分类；在PRD中预留接口逻辑和UI占位
-- **插件化架构**：开发侧将模块抽象，端侧重构图片处理管线，用GLSL写统一接口；工作量约多一周
-- **后端接口**：按标准RESTful加Swagger文档，便于后续迭代对接
+- **需求来源**：运营反馈希望下版本加AI修图快捷入口（一键去背景、智能调色）。
+- **本次不硬塞**：主线是性能和分类，硬塞风险大；在PRD预留接口逻辑和UI占位，开发侧做插件化架构。
+- **渲染管线重构**：开发2提出渲染层抽成插件化、用GLSL写统一接口，工作量多一周左右，需将非核心Bug修复后移腾资源。
+## 项目里程碑与内测计划
+- **里程碑**：按原定计划月底封版。
+- **内测包**：暂定下周三发，拉体验官群，重点跑AI分类和同步模块；产品做好反馈收集表，开发准备日志抓取。
 ## 结论与决定
-- **隐私相册入口**：提升至首部顶部二级菜单，产品出交互方案评审
-- **AI标签方案**：采用本地缓存策略加端侧预过滤，按需加载；开发1与开发2配合联调
-- **同步模块**：维持分片加载方案，每次拉50张，进度不能拖
-- **缩略图渲染**：采用新解码库优化，临时规避方案先稳住，正式修复排进V1.2
-- **时间轴优化**：采用本地索引预加载，注意与云同步模块资源隔离
-- **AI修图**：本次不实现，预留接口和插件化架构，非核心Bug修复往后排
-- **里程碑**：按原定计划月底封版，内测包暂定下周三发
+- **隐私相册入口**：提升至首部顶部二级菜单，产品出交互方案供评审。
+- **AI标签接口**：采用本地缓存策略加端侧预过滤、按需下载方案。
+- **同步模块**：按分片加载方案走，每次拉50张，进度不能拖。
+- **数据库锁死Bug**：用消息队列临时规避，正式修复排进V1.2迭代。
+- **时间轴优化**：加本地索引预加载，注意与云同步模块资源隔离。
+- **AI修图**：预留接口和UI占位，开发侧做插件化架构，非核心Bug修复后移。
+- **里程碑与内测**：月底封版，下周三发内测包。
 ## 行动项与分工
-- **发言人2（产品）**：下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查；制作AI修图占位图；准备反馈收集表；十一点半前将UI稿发给产品经理
-- **发言人3（开发1）**：下午拉分支改本地缓存逻辑，预计三天联调完；评估端侧预过滤模型体积和推理开销；按需加载预计两天完成；拉开发2配合端侧推理联调；今晚搭好接口联调环境，明天与测试过一遍；拉群与DBA对齐索引策略
-- **发言人4（开发2）**：今晚继续跑分片加载和渲染优化压测数据，明天同步；评估AI修图管线重构工作量，今天下班前发给产品经理
-- **产品经理**：周四参加UI走查；要求测试组将iOS和安卓性能报告合并为一份总览；调整非核心Bug优先级，资源给到管线重构和AI标签优化
+- **产品（发言人2）**：下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查；制作AI修图占位图；十一点半前将UI走查稿发给产品经理。
+- **开发1（发言人3）**：下午拉分支改本地缓存逻辑，预计三天联调完；评估端侧预过滤模型体积和端侧推理开销；按需下载约两天搞定；今晚搭好接口联调环境，明天与测试过一遍；拉群与DBA对齐索引策略。
+- **开发2（发言人4）**：今晚出性能报告初稿；继续跑分片加载和渲染优化压测数据，明天同步；评估管线重构精确工作量，今天下班前发给产品经理；让测试组将iOS和安卓对比数据合并成一份总览。
+- **产品经理（发言人1）**：下午两点参加UI走查；周四参加性能评审；要求开发1排联调时间，尽量周五前跑通主干流程。
 ## 待确认与风险
-- **端侧预过滤**：模型体积和端侧推理开销待评估；需申请200兆本地缓存空间，对安装包体积的影响待产品评估
-- **AI修图插件化**：具体实现方案待开发2评估工作量
-- **权限引导弹窗**：交互设计待产品出稿
-- **低端机掉帧**：上滑列表掉帧影响用户体验
-- **AI标签耗时**：单次请求从800毫秒涨至1.5秒，可能影响用户等待体验
-- **OOM崩溃**：同步队列积压超1000张时部分机型崩溃，iOS尤其严重
-- **数据库锁死**：批量删除照片时偶发，影响数据一致性
-- **时间轴卡死**：滑动到老照片卡死三秒以上，影响核心功能体验
-- **权限拒绝风险**：预加载需用户授权，若拒绝可能影响功能使用
-- **后台同步权限**：审核严，可能无法申请</t>
+- **本地缓存命中率低**时识别速度可能回溯，未明确应对方案。
+- **后台静默同步权限**申请被否，用户手动设置同步频率是否可行未确认。
+- **端侧预过滤**模型体积和端侧推理开销待评估；按需下载对安装包体积的影响待产品评估。
+- **预加载权限**引导弹窗交互设计待产品出稿。
+- **管线重构**工作量多一周，非核心Bug修复后移的具体范围待确认。
+- **风险**：低端机掉帧、AI接口耗时1.5秒、同步队列OOM崩溃、批量删除数据库锁死、时间轴卡死三秒以上、后台同步权限审核严。</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3605/4587</t>
+          <t>3605/4314</t>
         </is>
       </c>
     </row>
@@ -17518,87 +17562,97 @@
       <c r="C55" t="inlineStr">
         <is>
           <t># 全文摘要
-本次月度研讨会由总监主持，组长、销冠、销售A、销售B共同参与，围绕上月销售数据复盘与下月去化目标制定展开。会议覆盖销售数据复盘、工地开放日标准化、逼定策略、渠道带看管控、老带新政策、目标分解、专项培训及销控纪律等议题。核心结论为量够但转化不足，需重点提升逼定和转化环节，并明确下月总去化目标120套、工地开放日每周三固定开放、渠道带看实名制、周末业主答谢会联动去化等关键决定。上月案场总到访320组、成交76套、转化率23%，下月目标较上月增加50%。
+月度研讨会由总监主持，组长、销冠、销售A、销售B等案场团队参与，围绕上月转化率下滑问题展开。会议复盘了到访、成交、渠道占比等核心数据，分析了价格预期与交付信心两大客户流失抗性，并覆盖工地开放日、逼定策略、渠道管理、老带新、目标分解、培训与销控纪律等议题。最终确定下月去化120套目标，并部署工地开放日标准化、渠道带看实名制、周末答谢会联动去化等具体动作。关键锚点：转化率23%（环比降4个百分点）、渠道带看占比65%、下月目标120套（环比增50%）、老带新奖励2万元。
 # 分段速览
-## 00:00:00-00:01:17 开场与整体数据复盘
-总监宣布月度研讨会定于下午两点至两点四十，共四十分钟，指出上月市场波动大、项目整体去化尚可但部分数据不理想，要求组长先过核心指标。组长汇报后台完整数据：上月案场总到访三百二十组，环比增加百分之十五，数据达标；但成交七十六套，转化率百分之二十三，较上月百分之二十七下降四个百分点；渠道带看占比百分之六十五，自然来访仅百分之三十五；蓄客量约三千二百组，认购到成交流失率约百分之十八。总监总结为量够但卡在逼定和转化环节，并指出渠道带看比例过高意味着自主拓客和案场拦截能力在退化。
+## 00:00:00-00:01:17 开场与上月数据复盘
+总监开场定下会议时间下午两点至两点四十共四十分钟，指出上月市场波动大、项目整体去化尚可但部分数据不理想，要求组长先过核心指标。组长汇报后台完整数据：上月案场总到访三百二十组，环比增加百分之十五，达标；成交七十六套，转化率百分之二十三，较上月百分之二十七下降；渠道带看占比百分之六十五，自然来访百分之三十五；蓄客量约三千二百组，认购到成交流失率约百分之十八。总监总结为量够但转化不够，渠道占比过高反映自主拓客和案场拦截能力退化，点名销冠从一线实战角度分析客户流失原因。
 ## 00:01:53-00:03:36 客户流失抗性分析与工地开放日建议
-销冠复盘上月流失客户，集中在两个抗性：价格预期方面竞品推特价房、首付分期或送物业费，客户有心理落差；交付信心方面客户对园林选材、地下车库层高、外墙保温层等细节询问细致，怕买错，建议把工地实时进展和材料样板直接呈现。销售A分享改善型客户案例，带看三次并让客户直接问施工经理，客户因工程透明才定房，但工地开放日频率不够、陪看占时间影响转化。组长建议设固定节点，每周三下午固定开放，提前在客户群和朋友圈发预告，客户直接对接专属顾问。总监认可并要求组长出方案，定每周三、提前两天在CRM系统推送意向客户。
+销冠复盘上月流失客户，指出集中在两大抗性：价格预期方面竞品推特价房、首付分期、送物业费等玩法造成客户心理落差；交付信心方面客户对园林选材、地下车库层高、外墙保温层等细节存疑，怕买错，建议把工地实时进展和材料样板直接展示给客户。销售A补充称带改善型客户看房时叫上施工经理让客户直接问工人，客户因工程透明而定房，但工地开放日频率不够、客户自行看房不便、陪看占时间。组长反馈置业顾问反映工地开放日流程繁琐、报备审批要半天，建议设固定节点每周三下午开放，提前在客户群和朋友圈发预告，客户直接对接专属顾问。总监认可并要求组长出方案，将工地开放日标准化定在每周三，提前两天在CRM系统推送意向客户。
 ## 00:04:22-00:06:12 逼定策略与物料更新
-销冠分享逼定手法：不直接降价，而是算总账，将物业费、车位管理费、未来装修损耗拉表对比竞品，强调单价虽高两千但十年省下物业和品质维修维护费，再递上“限时权益”逼定函，承诺本周定下来亲自申请多送三年物业费，客户怕错过、看重确定性。销售B指出客户对“限时权益”不买账，需将权益具象化，如把三年缴费明细打印放在合同旁；同时反映案场物料更新慢，逼定函常是上月版本。组长记录物料问题，联系设计本周出新版，把权益条款写清楚，并计划下月制作“权益可视化”台卡放在洽谈区；同时指出跟进节奏慢，客户晚上问政策回复慢热度下降。
-## 00:06:12-00:08:27 跟进提速与渠道管控
-总监强调客户不过夜，要求分片包干：组长带销售A和销售B回访上周未成交的三百多组，重点盯“再考虑考虑”的客户；销冠梳理手头二十几个高意向客户，看能否周末逼定。针对渠道无效带看多、中介随便拉人凑数的问题，总监要求下月起带看必须实名登记并有明确需求标签，否则扣减渠道积分。销售A反映中介抵触，担心渠道不愿推盘，总监表示渠道部由他沟通，质量大于数量底线不能破，带看质量不行直接换备选。销售B汇报老带新进展：奖励政策为成功一套奖励两万现金或等值车位券，本月推四组、两组在谈，老业主需话术和礼品支持。组长准备定制伴手礼，包括高端茶叶礼盒和定制保温杯。
-## 00:08:43-00:10:08 老业主痛点与目标分解
-销冠指出老业主怕麻烦，建议搞“业主推荐官”活动，每成功推荐一套不仅给钱，还可升级物业服务等级，如优先预约维修、免费家政清洗一次，软性权益更易在小区群传播。总监认可软硬结合，要求组长下周前出详细执行表。随后总监宣布下月集团指标为总去化一百二十套，比上月多百分之五十。组长按人员配置和上月产出权重拆分：销冠目标二十八套，组长、销售A、销售B三人一组目标五十套，剩余十二套作为机动和渠道攻坚储备。总监确认拆分合理，但强调压力在销售A和销售B身上。
-## 00:10:19-00:12:10 表态与周末答谢会安排
-销售A表态能扛，手头有十五个准客户在等下周认筹通知，只要逼定话术统一、配合组长资源倾斜，五十套盘子三人能完成，但希望渠道带看质量再筛一筛。销售B计划周末搞小型业主答谢会，邀请已成交业主分享并推老带新政策，氛围好能提升转化率。销冠表示支持，可带人协助盯两桌，其改善型客户与答谢会客群重合度高，可做联动把高意向客户拢到一起周末集中去化。总监安排分工：销冠带人协助，销售B主抓流程，销售A负责客户邀约和逼定记录。同时宣布本周安排两次专项培训，分别为“竞品对比与抗性化解”和“逼定时机与谈判心理学”，每人必须参加，课后现场抽考，不过加练，组长盯进度并安排签到和考核表，结果挂钩下周绩效系数。
-## 00:12:29-00:15:07 销控纪律与会议总结
-组长提出销控表更新延迟，客户定后销售仍推同套房源易引起客诉。总监强调这是底线问题，要求销控实时同步，谁推哪套必须在群里喊一声、CRM系统同步锁房，下月再出现销控不同步丢单或客诉直接问责，组长定纪律并设专人每小时刷新销控大屏。组长总结五项核心议题：工地开放日周三固定开放、逼定权益可视化替换旧物料、渠道带看实名制与质量考核、周末业主答谢会联动去化、专项培训与销控纪律。销售A建议邀约话术统一为“老业主专属品鉴宴”，避开“促销”字眼，销售B随即修改邀约短信和电话模板。销冠补充逼定时财务和法务最好在洽谈区待命，现场能签当场出数出收据，客户安全感强，成交率能提至少两成。总监协调财务和法务周六日轮流值班在案场外围，要求组长散会后半小时内把会议纪要和任务分解表发到工作群，销冠下周晨会分享逼定案例，销售A、销售B盯紧周末答谢会，总监负责渠道和工程对接。
+总监提出价格抗性不能硬扛，下月政策调整，可在装修包和车位上做文章，询问销冠送三年物业费逼定手法的具体谈法。销冠说明不是硬谈而是换位算总账：把物业费、车位管理费、未来装修损耗拉表对比竞品，告知客户单价虽高两千但十年省下物业和品质维修维护费，再递上"限时权益"逼定函，承诺本周定亲自向营销总申请多送三年物业费，过了这周就没有，改善型客户看重确定性、最怕错过。销售B提出客户对"限时权益"不买账、觉得是套路，需把权益具象化，如将三年缴费明细打印出来放在合同旁，但案场物料更新慢、逼定函常是上月版本。组长记下物料问题，联系设计本周出新版、写清权益条款，并计划下月做"权益可视化"台卡放洽谈区，同时指出跟进节奏慢、客户晚上问政策回复慢导致热度下降。
+## 00:06:12-00:08:27 跟进提速与渠道管理
+总监强调客户不过夜、人手够就分片包干，要求组长带销售A和销售B回访上周未成交的三百多组客户，重点盯"再考虑考虑"的；销冠梳理手头二十几个高意向客户，看能否周末一波逼定。针对渠道无效带看多、中介随便拉人凑数的问题，总监要求下月起带看必须实名登记并有明确需求标签，否则扣减渠道积分。销售A表示中介较强势、称别的楼盘不查，担心查太严渠道不愿推盘，建议与渠道部通气。总监回应渠道部由他沟通，要精准客户不要凑人头，质量大于数量底线不能破，渠道带看质量不行直接换备选。随后询问销售B老带新推进情况，销售B汇报奖励政策已下来，成功一套奖励两万现金或等值车位券，本月推了四组、两组在谈，客户反馈好，但老业主不好意思开口，需提前给话术和礼品支持。
+## 00:08:27-00:11:20 老带新方案与下月目标分解
+组长准备定制伴手礼（楼盘周边高端茶叶礼盒、定制保温杯）供老业主转介绍时送。销冠提出老业主怕麻烦，建议搞"业主推荐官"活动，每成功推荐一套不仅给钱还可升级物业服务等级，如优先预约维修、免费家政清洗一次，软性权益更易在小区群传播。总监认可软硬结合，要求组长下周前出详细执行表。随后宣布集团下月总去化目标一百二十套，比上月多百分之五十。组长按人员配置和上月产出权重拆分：销冠目标二十八套，组长与销售A、销售B三人一组共五十套，剩余十二套作机动和渠道攻坚储备。销售A表态手头有十五个准客户等下周认筹通知，只要逼定话术统一、配合组长资源倾斜，五十套能扛下来，希望渠道带看质量再筛一筛。销售B计划周末办小型业主答谢会，邀请已成交业主分享并推老带新政策。销冠支持并称可协助盯两桌，其改善型客户与答谢会客群重合度高，可联动把高意向客户拢到一起周末集中去化。
+## 00:11:20-00:15:07 培训安排、销控纪律与收尾分工
+总监明确周末答谢会分工：销冠带人协助、销售B主抓流程、销售A负责客户邀约和逼定记录。本周安排两次专项演练，分别为"竞品对比与抗性化解"和"逼定时机与谈判心理学"，每人必须参加，课后现场抽考，不过加练，组长盯进度别流于形式。组长回应安排签到和考核表，结果挂钩下周绩效系数，并提出案场销控表更新延迟、客户定后销售仍推同套房易引起客诉。总监定性为底线问题，要求销控实时同步、群里喊一声、CRM系统同步锁房，再出现丢单或客诉直接问责，组长定纪律并设专人每小时刷新销控大屏。组长总结五项核心议题：优化工地开放日流程、逼定权益可视化、渠道带看实名制与质量考核、周末业主答谢会联动去化、专项培训与销控纪律。销售B补充答谢会邀约话术统一为"老业主专属品鉴宴"、避开"促销"字眼，随即去改邀约短信和电话模板。销冠建议逼定时财务和法务在洽谈区待命，现场签单出收据可提升成交率至少两成，总监协调财务法务周六日轮流值班在案场外围。总监收尾布置：组长散会后半小时内发会议纪要和任务分解表到工作群，销冠下周晨会分享逼定案例，销售A、销售B盯紧周末答谢会，总监本人盯渠道和工程对接。
 # 要点梳理
-## 上月销售数据复盘
-- **总到访**：上月案场总到访320组，环比增加15%，数据达标。
-- **成交与转化**：成交76套，转化率23%，较上月27%下降4个百分点。
-- **来访结构**：渠道带看占比65%，自然来访仅35%。
-- **蓄客与流失**：蓄客量约3200组，认购到成交流失率约18%。
-- **流失抗性**：客户流失集中在两个抗性——价格预期（竞品推特价房、首付分期、送物业费等）与交付信心（客户细问园林选材、车库层高、外墙保温层）。
-- **结论**：量够但转化不足，卡在逼定和转化环节，自主拓客能力和案场拦截能力退化。
-## 工地开放日标准化
-- **问题**：工地开放日频率不足，客户自行看房不便，陪看占用销售时间；报备审批流程繁琐，需半天。
-- **决定**：工地开放日定为每周三下午固定开放，提前两天在CRM系统推送意向客户，客户直接对接专属顾问，不走复杂流程。
-- **依据**：销售A分享改善型客户案例，三次带看均请施工经理现场答疑，客户因工程透明最终成交。
+## 上月案场数据复盘
+- **总到访**：320组，环比增加15%，达标
+- **成交与转化率**：成交76套，转化率23%，较上月27%下降4个百分点
+- **渠道结构**：渠道带看占比65%，自然来访35%
+- **蓄客与流失**：蓄客量约3200组，认购到成交流失率约18%
+- **销冠业绩**：上月成交19套，为组内最高
+- **总监判断**：量够但卡在逼定和转化环节，渠道占比过高反映自主拓客和案场拦截能力退化
+## 客户流失抗性分析
+- **价格预期抗性**：竞品推特价房、首付分期、送物业费等玩法，客户心理有落差
+- **交付信心抗性**：客户对园林选材、车库层高、外墙保温层等细节存疑，怕买错
+- **工程透明案例**：销售A带改善型夫妻档三次看房，每次叫上施工经理让客户直接问工人，客户因工程透明而定房
+- **工地开放日问题**：频率不足，客户自行看房不便，陪看占时间；流程繁琐，报备审批需半天
 ## 逼定策略与权益可视化
-- **销冠方法**：不直接降价，采用“算总账”方式——将物业费、车位管理费、装修损耗拉表对比竞品，说明单价虽高2000元但十年省下物业和品质维修维护费；配合“限时权益”逼定函，承诺本周定下可申请多送三年物业费。
-- **销售B补充**：客户对“限时权益”不买账，需将权益具象化——把三年缴费明细打印放在合同旁。
-- **物料问题**：现场逼定函常为上月版本，组长已记录，联系设计本周出新版，写清权益条款避免歧义；下月制作“权益可视化”台卡放洽谈区。
-## 渠道带看质量管控
-- **问题**：渠道带看量上升但无效带看多，多为中介随便凑数。
-- **决定**：下月起带看必须实名登记，需明确需求标签，否则扣减渠道积分；质量不行直接换备选。
-- **风险**：销售A反馈中介抵触，称其他楼盘不查此要求，怕渠道不愿推盘；总监表示亲自与渠道部沟通，质量大于数量底线不破。
-## 老带新政策与业主答谢会
-- **奖励政策**：老带新成功一套奖励两万现金或等值车位券。
-- **当前进展**：销售B本月推四组，两组在谈，客户反馈老业主有面子、奖励实在；老业主不好意思开口，需提前给话术和礼品支持。
-- **伴手礼**：组长准备定制高端茶叶礼盒和保温杯，老业主转介绍时直接送。
-- **业主推荐官活动**：销冠建议每成功推荐一套，除现金外升级物业服务等级（优先预约维修、免费家政清洗一次），软性权益更易在小区群传播。
-## 下月目标分解与专项培训
-- **总目标**：集团指标下月总去化120套，比上月多50%。
-- **拆分**：销冠28套；组长、销售A、销售B三人一组共50套；剩余12套作为机动和渠道攻坚储备。
-- **表态**：销售A手头15个准客户等下周认筹通知，需逼定话术统一和组长资源倾斜；销售B计划周末办小型业主答谢会，邀请成交业主分享并推老带新政策。
-- **培训安排**：本周两次专项演练——“竞品对比与抗性化解”“逼定时机与谈判心理学”，每人必须参加，课后现场抽考，不过加练；组长安排签到和考核表，结果挂钩下周绩效系数。
-## 销控纪律与流程优化
-- **问题**：销控表更新延迟，客户定后销售仍推同套房源，易引起客诉。
-- **决定**：销控必须实时同步，谁推哪套在群里喊一声，CRM系统同步锁房；下月再出现销控不同步丢单或客诉直接问责。
-- **执行**：组长在晨会上强调，设置专人每小时刷新销控大屏。
-## 会议总结与后续安排
-- **邀约话术**：销售A建议统一为“老业主专属品鉴宴”，避开“促销”字眼，客户抵触心理小；销售B即改邀约短信和电话模板。
-- **财务法务待命**：销冠建议逼定时财务和法务在洽谈区待命，现场能签当场出数出收据，成交率可提升至少两成；总监协调周六日轮流值班在案场外围。
-- **会后任务**：组长散会后半小时内发会议纪要和任务分解表到工作群；销冠下周晨会分享逼定案例。
+- **算总账法**：销冠不直接降价，拉表对比物业费、车位管理费、装修损耗，说明单价高2000元但十年省物业和品质维修维护费
+- **限时权益逼定**：销冠递送逼定函，承诺本周定亲自申请多送三年物业费，过了本周没有
+- **权益具象化难点**：销售B发现客户对限时权益不买账，改为把三年缴费明细打印出来放合同旁
+- **物料滞后问题**：逼定函常是上月版本，现场案场物料更新慢
+## 跟进节奏与渠道管理
+- **跟进节奏问题**：客户晚上问政策回复慢，热度下降
+- **回访要求**：总监要求客户不过夜，组长带销售A和销售B分片包干，回访上周未成交的300多组客户，重点盯「再考虑考虑」的
+- **高意向客户梳理**：销冠梳理手头二十几个高意向客户，争取周末一波逼定
+- **渠道无效带看**：中介随便拉人凑数，渠道费白给
+- **渠道实名制决定**：下月起带看必须实名登记，需明确需求标签，否则扣减渠道积分
+- **中介抵触风险**：销售A担心中介说别的楼盘不查，怕渠道不愿推盘；总监表示亲自与渠道部沟通，质量大于数量，不行直接换备选
+## 老带新政策与业主推荐官
+- **奖励政策**：老带新成功一套奖励2万现金或等值车位券
+- **当前进展**：销售B本月推4组，2组在谈，客户反馈良好
+- **老业主痛点**：不好意思开口，需提前给话术和礼品支持
+- **伴手礼准备**：组长准备定制高端茶叶礼盒和定制保温杯，老业主转介绍时直接送
+- **业主推荐官活动**：销冠建议每成功推荐一套，除现金外升级物业服务等级（优先预约维修、免费家政清洗一次），软性权益更易在小区群传播
+## 下月目标分解与团队分工
+- **总目标**：集团下月总去化120套，比上月多50%
+- **目标拆分**：销冠28套；组长+销售A+销售B共50套；机动和渠道攻坚12套
+- **销售A储备**：手头15个准客户，等下周认筹通知，表态50套盘子三人能扛
+- **销售B计划**：周末办小型业主答谢会，邀请成交业主分享并推老带新政策
+- **销冠联动**：销冠协助盯两桌，其改善型客户与答谢会客群重合度高，可把高意向客户拢到一起周末集中去化
+## 专项培训与销控纪律
+- **培训安排**：本周两次专项演练——「竞品对比与抗性化解」「逼定时机与谈判心理学」，每人必须参加
+- **考核机制**：课后现场抽考，过不了加练，结果挂钩下周绩效系数
+- **销控表问题**：更新延迟，客户定后销售仍推同套房，易引起客诉
+- **销控纪律**：总监要求实时同步，谁推哪套在群里喊一声，CRM系统同步锁房；再出现丢单或客诉直接问责
+- **刷新机制**：组长设置专人每小时刷新销控大屏，晨会强调
+## 周末答谢会与现场服务
+- **邀约话术调整**：销售A建议统一为「老业主专属品鉴宴」，避开「促销」字眼，客户抵触心理小
+- **话术模板修改**：销售B负责改邀约短信和电话模板
+- **财务法务前置**：销冠建议财务和法务在洽谈区待命，现场签单出收据，客户安全感强，成交率可提升至少两成
+- **值班安排**：总监协调财务和法务周六日轮流值班，在案场外围
+- **答谢会分工**：销冠带人协助，销售B主抓流程，销售A负责客户邀约和逼定记录
 ## 结论与决定
-- 工地开放日定为每周三下午固定开放，提前两天在CRM系统推送意向客户。
-- 逼定权益可视化，本周内更新逼定函物料，下月制作权益可视化台卡。
-- 渠道带看必须实名登记并明确需求标签，否则扣减渠道积分。
-- 下月总去化目标120套：销冠28套，组长、销售A、销售B三人组50套，剩余12套机动。
-- 周末举办业主答谢会，销售B主抓流程，销售A负责邀约和逼定记录，销冠带人协助。
-- 销控必须实时同步，CRM系统同步锁房，下月再出现销控不同步丢单或客诉直接问责。
-- 财务和法务周六日轮流值班在案场外围。
+- **工地开放日标准化**：定在每周三，提前两天在CRM系统推送给意向客户，直接约看、直接问、直接签
+- **逼定权益可视化**：本周内更新逼定函物料，制作「权益可视化」台卡放洽谈区
+- **渠道带看实名制**：下月起必须实名登记并需明确需求标签，否则扣减渠道积分
+- **老带新方案**：加入业主推荐官活动，软硬结合，下周前出详细执行表
+- **下月目标**：总去化120套，拆分销冠28套、组长+销售A+销售B共50套、机动和渠道攻坚12套
+- **销控纪律**：CRM系统锁房，再出现丢单或客诉直接问责
 ## 行动项与分工
-- **组长**：制定工地开放日标准化方案（每周三固定开放、提前两天CRM推送）；联系设计本周出新版逼定函；准备定制伴手礼；设置专人每小时刷新销控大屏；散会后半小时内发会议纪要和任务分解表到工作群。
-- **销冠**：梳理手头二十几个高意向客户，周末配合答谢会带人协助；下周晨会分享逼定案例。
-- **销售A**：周末答谢会负责客户邀约和逼定记录；配合组长回访上周未成交客户；统一邀约话术为“老业主专属品鉴宴”。
-- **销售B**：周末答谢会主抓流程；修改邀约短信和电话模板；推进老带新业务。
-- **总监**：与渠道部沟通实名制要求；协调财务和法务周六日值班。
+- **组长**：出工地开放日标准化方案；联系设计本周出新版逼定函；准备定制伴手礼；出老带新详细执行表（下周前）；安排培训签到和考核表；设置专人每小时刷新销控大屏；散会后半小时内把会议纪要和任务分解表发工作群
+- **销冠**：梳理二十几个高意向客户，周末配合答谢会联动去化；协助答谢会盯两桌；下周晨会分享逼定案例
+- **销售A**：梳理客户池，周末答谢会负责客户邀约和逼定记录
+- **销售B**：改邀约短信和电话模板为「老业主专属品鉴宴」；周末答谢会主抓流程；推进老带新
+- **总监**：与渠道部沟通带看实名制；协调财务和法务周六日轮流值班；盯渠道和工程对接
 ## 待确认与风险
-- 渠道带看质量差、无效带看多，可能影响转化。
-- 中介对实名制有抵触，可能影响渠道推盘意愿。
-- 现场物料更新慢，逼定函版本滞后可能影响逼定效果。
-- 销控表更新延迟可能引起客诉。</t>
+- **渠道实名制执行**：中介可能抵触，需与渠道部沟通确认执行细节，总监表示质量大于数量、不行换备选
+- **周末答谢会**：具体流程和物料准备尚未细化
+- **转化率下滑**：从27%降至23%，影响整体去化
+- **渠道依赖**：带看占比65%，自主拓客和案场拦截能力退化
+- **交付信心不足**：客户担心买错，需持续工程透明化
+- **销控延迟风险**：更新不及时可能引起客诉</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>66</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4211/4712</t>
+          <t>4211/5027</t>
         </is>
       </c>
     </row>
@@ -17675,75 +17729,73 @@
       <c r="C56" t="inlineStr">
         <is>
           <t># 全文摘要
-本次团队例会由组长主持，A与B两位成员参与，主要同步ASR模型迭代进度，并解决线上推理延迟与长音频卡死问题。会议围绕数据清洗与模型训练、推理延迟优化、长音频卡死修复、监控与自动化评估体系建设、前端采样率升级五个板块展开。关键结论为：确认流式RNN-T混合架构与2秒切分方案，稳定性优先、精度次之，下周先出热修复版本上灰度。关键数字锚点：有效语音时长占比从89%提升至94%，验证集WER下降0.8个百分点，首字延迟目标控制在80ms以内，热修复版本周四提测。
+本次团队例会由组长主持，A与B两位成员参与，主要同步ASR模型迭代进度，并协调线上推理延迟与长音频卡死问题的解决资源。会议覆盖数据清洗与模型训练、推理延迟优化、长音频卡死修复、监控与自动化评估体系建设、前端32k采样率升级五个议题。数据清洗流水线完成第二轮，有效语音时长占比从89%提升至94%，验证集WER下降0.8个百分点；推理侧确定改为静态分段加流式解码方案，目标首字延迟控制在80ms以内；针对线上解码器loop卡死问题，决定增加early stopping机制，热修复版本周四提测、下周灰度。组长明确稳定性优先、精度次之，并协调下周一划拨三块A100用于增量训练。
 # 分段速览
-## 00:00:00-00:00:58 开场与数据训练进展
-组长开场明确会议目标：过一遍上周ASR模型迭代进度、线上推理延迟和长音频卡死问题，要求A和B分别同步各自板块现状并直接提出卡点或资源需求。A汇报数据清洗流水线已完成第二轮，将长尾噪音、极端口音和背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%左右；同时重新校对CTC的blank token分布，发现多音字和连读场景切分点存在偏移，计划用新基准跑一轮消融。B反馈验证集WER下降约0.8个百分点，但指出低资源语言混合边界场景下切分仍有毛刺，中英文切换时模型容易吞掉过渡音或重复解码。
-## 00:00:58-00:02:55 架构调整与显存评估
-A回应边界切分问题源于CTC对齐阶段对跨语言边界和轻声尾音处理不够平滑，计划将全纯Transformer架构换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练；数据增强策略已加入时间偏移，但对背景白噪声和混响鲁棒性不足，准备引入MixUp和CutMix再迭代。B认可混合架构方向，但提出RNN-T缓存机制和显存占用问题——GPU集群虽为A100，并发量上升时KV Cache显存峰值容易飙高，可能导致线上服务OOM。A回应已评估该问题，计划对RNN-T的prefix LM缓存做INT8量化并配合动态缓存释放策略，预计压降30%左右显存占用，但压测数据尚未跑完，明天下午将日志和截图发群里同步阈值。
+## 00:00:00-00:00:58 开场与数据训练汇报
+组长开场说明会议目的：过一遍上周ASR模型迭代进度，以及线上推理延迟和长音频卡死问题，要求A和B分别同步各自板块现状，有卡点或资源需求直接提。A汇报数据清洗流水线已跑完第二轮，将长尾噪音、极端口音和背景人声重叠片段分流处理，有效语音时长占比从89%提升至94%左右；同时重新校对了CTC的blank token分布，发现多音字和连读场景切分点有偏差，计划用新基准跑消融实验。
+## 00:00:58-00:02:55 验证集表现与架构切换讨论
+B反馈数据质量提升后验证集WER下降约0.8个点，但低资源语言混合边界场景下切分仍有毛刺，中英文切换时模型易吞音或重复解码。A回应称是CTC对齐阶段对跨语言边界和轻声尾音处理不够平滑，计划将全纯Transformer架构换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练；数据增强已加时间偏移，但白噪声和混响鲁棒性不足，准备引入MixUp和CutMix迭代。B提醒评估RNN-T的缓存机制和显存占用，并发量高时KV Cache显存峰值易飙高，可能导致服务OOM。A回应已评估，计划对prefix LM缓存做INT8量化配合动态缓存释放策略，预计压降30%左右显存占用，压测数据明天下午发群里。
 ## 00:02:55-00:04:35 推理延迟优化方案
-B汇报推理侧卡点集中在动态Batching调度逻辑：线上请求长短音频混排，现有队列切分导致首字延迟波动在150ms到300ms之间，产品反馈体验不连贯。计划将动态Batching改为静态分段加流式解码组合方案——音频按2秒切块，前端VAD预过滤，后端用RNN-T增量解码，目标首字延迟控制在80ms以内，整体吞吐量稳定在120路并发。VAD阈值暂定-25dB，结合能量和谱熵双模型判断，但真实线上底噪更复杂，下周将拉线上流量回放做端到端对比。A提醒VAD阈值需平衡误切率和漏切率，阈值过高会切掉轻声尾音导致缺字，过低则产生多余切分增加无效推理，并要求拉回放时打点前后帧特征日志以便排查切分点对齐影响。
-## 00:04:35-00:06:43 组长指导意见与自动化评估
-组长确认调整方向并提出三点要求：流式架构切换不能影响现有非流式离线批处理，双线都要保且测试用例覆盖全；VAD阈值由B做消融实验，画误切率和漏切率曲线找最优解；A的模型训练算力已协调，下周一开始划拨三块A100做增量训练，需注意与NLP组错峰使用。A回应将离线和流式验证集分开跑，测试用例周五前发评审，并调整启动脚本优先跑验证集小的实验、大训练放周末夜间；同时提出用GitLab CI搭建自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码、结果对比，WER未下降或RTF超标直接打回。组长认可并要求B将压测脚本也挂上去形成闭环，A预计三天完成，周四前出V1版本，B配合将压测数据输出为标准JSON格式。
+B说明推理侧卡点是动态Batching调度逻辑，长短音频混排导致首字延迟波动在150ms到300ms之间，产品反馈体验不连贯。计划改为静态分段加流式解码组合方案：音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，目标首字延迟控制在80ms以内，整体吞吐量稳定在120路并发。VAD阈值暂定-25dB，结合能量和谱熵双模型判断，下周拉线上流量回放做端到端对比。A提醒VAD阈值需平衡误切率和漏切率，阈值过高会切掉轻声尾音导致缺字，过低则增加无效推理，要求打点前后帧特征日志便于排查切分点对齐影响。
+## 00:04:50-00:06:43 组长指示与自动化评估
+组长提三点要求：流式架构切换不能影响非流式离线批处理，测试用例需覆盖全；VAD阈值由B做消融实验画误切率和漏切率曲线找最优解；下周一开始划拨三块A100给增量训练，注意与NLP组错峰排队。A回应将离线和流式验证集分开跑，测试用例周五发评审，并调整启动脚本优先跑验证集小的实验。A补充提出用GitLab CI搭建自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码、结果对比，WER未降或RTF超标直接打回，预计三天完成、周四前出V1版本。组长认可并要求B的压测脚本也挂上去形成闭环，B配合将压测数据输出为标准JSON格式。
 ## 00:06:43-00:08:49 长音频卡死问题与热修复
-B报告线上特殊场景报错：用户输入超长连续且带方言口音的音频时，解码器陷入无效循环导致loop卡死，直接触发服务器节点重启。当前解码器默认max steps为2048个token、超时5秒，但部分音频解码序列长度超阈值后解码器未做优雅降级直接OOM，日志显示RNN-T的attention权重一直震荡未收敛。A建议增加early stopping机制，结合置信度阈值和连续低概率token判断——连续30步置信度低于0.2时强制截断并返回当前序列，预计能解决90%以上卡死问题。B将实现该逻辑并配合超时熔断和降级返回，同时询问输出序列长度受限是否影响专业术语或长句完整识别。组长明确稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度，B今晚改完周四提测，A配合长序列数据配比和边界用例验证。
-## 00:08:49-00:10:56 监控体系与采样率升级
-B提出日志系统过于简陋，线上推理的中间特征和中间帧无法落盘，排查问题全靠猜测，计划接入Prometheus和Grafana监控面板，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标。组长认可需求并协助对接运维，要求明天下班前出监控指标定义文档，告警阈值分P0和P1两级——P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增。随后B指出前端SDK音频采样率仍为16k而新模型为32k输入，前端不升级则上采样会引入高频伪影影响识别率，前端对接人称排期推至下月。组长表示32k模型在长尾词上WER比16k好0.5%，将拉产品和技术总监优先插队推进；备选方案为服务端加实时重采样模块做兼容但会增加CPU开销。A建议先由B写轻量级重采样插件用libresample实测CPU占用和延迟影响再决策，B同意先出压测对比数据，CPU开销控制在5%以内再提方案。
-## 00:10:56-00:11:57 总结与收尾
-组长总结今日要点：第一，流式RNN-T混合架构和2秒切分方案由A和B分头推进，本周五前出详细设计和压测数据；第二，VAD阈值和长序列解码卡死问题，B周四出消融报告和热修复方案，A配合长序列数据配比和评估流水线对接；第三，前端32k采样率升级，B出对比文档和重采样插件实测，组长拉会推进；第四，监控面板和CI自动评估流水线本周内定稿并开始对接运维和测试环境。A确认周三前将CI脚本和测试用例发群里评审，B确认负责推理优化、VAD消融、热修复和监控文档，会议结束。
+B报告线上特殊场景：用户输入超长连续带方言口音音频时，解码器陷入无效循环导致loop卡死，服务器节点重启。解码器默认max steps为2048个token、超时5秒，但实际序列超长时未优雅降级直接OOM，原因是RNN-T的attention权重震荡未收敛。A建议加early stopping机制：连续30步置信度低于0.2时强制截断并返回当前序列，能解决90%以上卡死问题。B将实现该逻辑并配合超时熔断和降级返回。组长指示稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度，B今晚改完、周四提测，A配合长序列数据配比和边界用例验证。
+## 00:08:49-00:11:57 监控体系与前端采样率升级
+B提出日志系统简陋，中间特征和中间帧无法落盘，申请接入Prometheus和Grafana监控面板，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标。组长认可并要求出监控指标定义文档，告警阈值分P0（服务不可用或延迟超500ms）和P1（显存超85%或WER突增）两级。B另报告前端SDK采样率仍为16k而新模型为32k输入，不升级会引入高频伪影影响识别率，前端排期推至下月。组长决定拉产品和技术总监过一下优先插队，32k模型在长尾词上比16k好0.5%的WER；若前端坚持不升级，可在服务端加实时重采样模块但会增加CPU开销。A建议先写轻量级重采样插件用libresample实测CPU占用和延迟影响再决策，B将CPU开销控制在5%以内再提方案。组长总结四项任务分工，确认无其他卡点后散会。
 # 要点梳理
 ## 数据清洗与模型训练
-- **数据清洗**：混合语料库清洗流水线完成第二轮，长尾噪音、极端口音、背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%
-- **WER表现**：验证集WER下降0.8个百分点；低资源语言混合边界场景下，中英文切换时模型易吞音或重复解码
-- **架构调整**：计划将全纯Transformer架构更换为流式RNN-T与Transformer混合形态，先在20小时核心数据上训练
-- **数据增强**：已加入时间偏移，对背景白噪声和混响鲁棒性不足，准备引入MixUp和CutMix再迭代一轮
-- **CTC对齐**：重新校对blank token分布，发现多音字和连读场景切分点有偏移，本周用新基准跑消融
+- **数据清洗**：混合语料库清洗流水线完成第二轮，长尾噪音、极端口音、背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%。
+- **标注对齐**：重新校对CTC的blank token分布，发现多音字和连读场景切分点偏，计划用新基准跑一轮消融。
+- **WER表现**：验证集WER下降0.8个百分点；低资源语言混合边界场景下，中英文切换时模型易吞音或重复解码。
+- **架构切换**：计划将全纯Transformer架构换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练。
+- **数据增强**：已加时间偏移，对背景白噪声和混响鲁棒性不足，准备引入MixUp和CutMix再迭代一轮。
+- **显存评估**：RNN-T的prefix LM缓存拟做INT8量化配合动态缓存释放策略，预计压降30%显存占用；具体显存曲线和压测数据未跑完，明天下午发日志和截图确认阈值。
 ## 推理延迟优化
-- **现状问题**：动态Batching在长短音频混排时首字延迟波动在150ms到300ms之间，产品反馈体验不连贯
-- **调整方案**：改为静态分段加流式解码组合方案——音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码
-- **性能目标**：首字延迟控制在80ms以内，整体吞吐量稳定在120路并发
-- **VAD阈值**：暂定-25dB，结合能量和谱熵双模型判断；需平衡误切率和漏切率，阈值过高切掉轻声尾音致缺字，过低增加无效推理
-- **验证计划**：下周拉线上流量回放做端到端对比，前后帧特征打点日志便于排查切分点对齐影响
-- **显存评估**：RNN-T的prefix LM缓存拟做INT8量化配合动态缓存释放策略，预计压降30%左右显存占用；压测日志和截图明天下午发群同步阈值
+- **现状问题**：动态Batching在长短音频混排时首字延迟波动在150ms至300ms之间，产品反馈体验不连贯。
+- **调整方案**：改为静态分段加流式解码组合——音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码；目标首字延迟控制在80ms以内，整体吞吐量稳定在120路并发。
+- **VAD阈值**：暂定-25dB，结合能量和谱熵双模型判断；需平衡误切率和漏切率，阈值过高切掉轻声尾音致缺字、过低增加无效推理。
+- **验证计划**：下周拉线上流量回放做端到端对比，前后帧特征打点日志便于排查切分点对齐影响。
+- **组长要求**：流式架构切换不能影响非流式离线批处理，双线都要保，测试用例需覆盖全；VAD阈值做消融实验画误切率和漏切率曲线找最优解。
 ## 长音频卡死问题
-- **故障现象**：线上超长连续带方言口音音频导致解码器loop卡死，陷入无效循环，直接触发服务器节点重启
-- **参数现状**：解码器默认max steps为2048个token，超时时间5秒；部分音频解码序列超阈值，解码器未做优雅降级直接报OOM
-- **根因分析**：RNN-T的attention权重持续震荡未收敛
-- **修复方案**：增加early stopping机制——连续30步置信度低于0.2时强制截断并返回当前序列，预计解决90%以上卡死问题；同时实现超时熔断和降级返回
-- **处理原则**：组长明确稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度
-## 监控与自动化评估
-- **监控面板**：接入Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标
-- **告警分级**：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增；监控指标定义文档明天下班前发组长，由组长转发运维负责人
-- **CI评估流水线**：用GitLab CI实现代码合入即触发数据拉取、模型加载、测试集解码、结果对比；WER未下降或RTF超标直接打回
-- **落地时限**：A负责评估脚本和流水线配置，预计三天，周四前出V1版本；B配合将压测数据输出为标准JSON格式
-## 前端采样率升级
-- **问题**：前端SDK音频采样率16k，新模型输入32k，上采样引入高频伪影影响识别率；32k模型在长尾词上WER比16k好0.5%
-- **排期冲突**：前端对接人称排期推至下个月
-- **推进方案**：B出对比文档和重采样插件实测（用libresample，CPU开销控制在5%以内），组长拉产品和技术总监优先插队；备选方案为服务端加实时重采样模块，但会增加CPU开销和推理链路延迟
+- **问题现象**：线上超长连续带方言口音音频导致解码器loop卡死、服务器节点重启；解码器默认max steps为2048个token、超时5秒，实际序列超长时未优雅降级直接OOM。
+- **根因**：RNN-T的attention权重持续震荡未收敛。
+- **修复方案**：增加early stopping机制——连续30步置信度低于0.2时强制截断并返回当前序列，预计解决90%以上卡死问题；同时配合超时熔断和降级返回。
+- **组长指示**：稳定性优先、精度次之，专业术语后续靠词表扩展和热词注入解决；下周先出热修复版本上灰度。
+- **分工**：B负责改解码逻辑，A配合长序列数据配比和边界用例验证。
+## 监控与自动化评估体系
+- **监控面板**：计划接入Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标；监控指标定义文档明天下班前发组长，由组长转发运维负责人。
+- **告警分级**：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增。
+- **CI自动评估**：用GitLab CI跑自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码、结果对比；WER未下降或RTF超标直接打回；预计三天完成，周四前出V1版本。
+- **闭环要求**：组长要求B的压测脚本也挂到流水线，压测数据输出为标准JSON格式方便流水线读取。
+## 前端32k采样率升级
+- **现状**：前端SDK采样率仍为16k，新模型为32k输入，不升级会引入高频伪影影响识别率；32k模型在长尾词上比16k好0.5%的WER。
+- **排期冲突**：前端对接人称排期推至下月；组长决定拉产品和技术总监过一下，优先插队。
+- **备选方案**：若前端坚持不升级，考虑服务端加实时重采样模块但会增加CPU开销；A建议B先写轻量级重采样插件用libresample实测CPU占用和延迟影响，CPU开销控制在5%以内再提方案。
 ## 结论与决定
-- **稳定性优先，精度次之**：长音频卡死问题先出热修复版本上灰度，专业术语识别后续通过词表扩展和热词注入解决
-- **架构方向确认**：流式RNN-T混合架构和2秒切分方案方向可行，但流式架构切换不能影响现有非流式离线批处理，双线都要保，测试用例需全覆盖
-- **算力协调**：组长协调下周一划拨三块A100做增量训练，需与NLP组错峰使用，注意调度面板排队
+- 流式RNN-T混合架构和2秒切分方案，A和B分头推进，本周五前出详细设计和压测数据。
+- VAD阈值和长序列解码卡死问题，B周四出消融报告和热修复方案，A配合长序列数据配比和评估流水线对接。
+- 前端32k采样率升级，B出对比文档和重采样插件实测，组长拉会推进。
+- 监控面板和CI自动评估流水线，本周内定稿并开始对接运维和测试环境。
+- 稳定性优先、精度次之，下周先出热修复版本上灰度；流式架构切换不能影响非流式离线批处理。
 ## 行动项与分工
-- **A**：本周五前出流式RNN-T混合架构详细设计和压测数据；周三前把CI脚本和测试用例发群评审；周四前出评估流水线V1版本；配合长序列数据配比和边界用例验证
-- **B**：今晚改完热修复版本，周四提测；周四出VAD阈值消融报告和热修复方案；明天下班前发监控指标定义文档；出前端32k对比文档和重采样插件实测
-- **组长**：明天拉产品和技术总监过前端32k采样率升级事项；将监控指标文档转发运维负责人
-- **算力调度**：A调整启动脚本，优先跑验证集小的实验，大训练放周末夜间，避开NLP组四个排队job
+- **A**：周三前把CI脚本和测试用例发群里评审；周四前出自动评估流水线V1版本；周五前出流式架构详细设计；配合长序列数据配比和边界用例验证。
+- **B**：今晚改完热修复版本解码逻辑，周四提测；周四出VAD消融报告；明早发监控指标定义文档；出前端32k对比文档和重采样插件实测。
+- **组长**：下周一开始划拨三块A100给增量训练，注意与NLP组错峰；明天拉产品和技术总监过前端升级排期；转发监控指标文档给运维负责人。
 ## 待确认与风险
-- **显存压测未完成**：RNN-T的prefix LM缓存INT8量化配合动态缓存释放策略的具体显存曲线和压测数据未跑完，明天下午发群同步阈值
-- **VAD阈值待验证**：-25dB阈值在真实线上底噪环境下是否最优，需通过线上流量回放验证误切率与漏切率平衡
-- **热词注入影响待确认**：流式解码和静态切分的衔接是否影响热词注入的实时生效，待技术细节验证
-- **服务端重采样待决策**：是否采用服务端实时重采样模块需B先出压测对比数据（CPU开销控制在5%以内）再决策
-- **OOM风险**：并发量上升时KV Cache显存峰值易飙高，可能导致服务OOM
-- **算力冲突**：与NLP组项目存在GPU排队撞车风险，需错峰运行</t>
+- RNN-T的prefix LM缓存INT8量化配合动态缓存释放策略，具体显存曲线和压测数据未跑完，需明天下午发日志和截图确认阈值。
+- VAD预过滤阈值-25dB在真实线上环境的底噪下是否合适，需下周拉线上流量回放做端到端对比确认。
+- 流式解码和静态切分的衔接是否影响热词注入的实时生效，待技术细节验证。
+- 前端32k采样率升级排期能否提前，需组长拉会与产品和技术总监确认。
+- 算力资源与NLP组排队冲突，需错峰使用；服务端加重采样模块可能增加CPU开销和推理延迟。</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>68.7</v>
+        <v>72.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3912/4913</t>
+          <t>3912/4490</t>
         </is>
       </c>
     </row>

--- a/now.xlsx
+++ b/now.xlsx
@@ -567,58 +567,57 @@
       <c r="C2" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲，围绕今年慕安会报告主题“走向多极化”，阐述中国推动平等有序的世界多极化的主张。演讲提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢，并强调中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。关键数字锚点包括：联合国会员国从80年前的51个增至193个、中国承担超过20%的联合国会费、去年中国GDP增长5%且对世界经济增长贡献率接近30%。问答环节涉及国际秩序与规则、乌克兰危机、中美关系等议题，会后王毅将前往纽约出席联合国安理会会议。
+王毅在慕尼黑安全会议上发表演讲并回答提问，围绕世界走向多极化这一主题，提出中国主张推动平等有序的世界多极化，并阐述四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。演讲中提及关键数字：80年前联合国成立时只有51个会员国，到今天有193个国家；中国承担超过20%的联合国会费；去年中国GDP增长5%，对世界经济增长的贡献率接近30%。问答环节涉及国际秩序与规则、乌克兰危机、中美关系等议题，王毅回应称中国是现行国际秩序的受益者，主张维护以联合国为核心的国际体系；中国同俄罗斯建立了不结盟、不对抗、不针对第三方的睦邻友好关系，将继续劝和促谈；中方愿意按照相互尊重、和平共处、合作共赢三原则同美方构建稳定健康可持续的双边关系。
 # 核心信息
-## 多极化世界秩序与中国主张
-- **世界走向多极化**：80年前联合国成立时仅51个会员国，至今已有193个国家；多极化的世界既是历史必然，也正在成为现实。
-- **中国主张平等有序的世界多极化**：这是习近平主席提出的重大主张，中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。
-- **四点看法**：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢；坚持权利平等、机会平等、规则平等应成为建设多极世界的基本原则。
-- **中国参与国际体系数据**：加入几乎所有普遍性的政府间国际组织和600多项国际公约；承担超过20%的联合国会费；建成世界上最大的清洁发电体系；切实履行《巴黎协定》。
-- **全球治理倡议**：提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
+## 多极化主张
+- **世界走向多极化**：80年前联合国成立时仅51个会员国，如今已有193个国家；王毅借2025年慕安会报告主题指出世界正走向多极化，中国主张推动**平等有序的世界多极化**，并称中国必将是多极体系中的确定性因素、坚定做变革世界中的建设性力量。
+- **四点看法**：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，以联合国宪章宗旨和原则为根本遵循，反对实力至上、丛林法则和双重标准；三是践行多边主义，倡导共商共建共享的全球治理观；四是坚持开放共赢，以普惠包容的经济全球化支撑平等有序的世界多极化。
+## 国际法治与多边主义
+- **维护国际法治**：中国加入了几乎所有普遍性的政府间国际组织和**600多项国际公约**，从不搞例外主义，更不搞合则用、不合则弃；在遵守国际法上不能搞双重标准，要尊重各国主权和领土完整，就应该支持中国实现完全统一。
+- **践行多边主义**：联合国是践行多边主义、推进全球治理的核心平台，已为各国遮风挡雨80年；中国坚定维护联合国权威和地位，承担**超过20%的联合国会费**，切实履行《巴黎协定》，建成世界上最大的清洁发电体系。
+- **全球治理公共产品**：中国提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
+## 开放共赢
+- **经济发展数据**：2024年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**，担当全球经济增长的重要引擎，向世界释放超大规模市场红利。
+- **国际合作**：中国愿推动高质量共建“一带一路”，同欧盟的“全球门户”战略相互对接；今年是中欧建交50周年，中方愿同欧方深化战略沟通和互利合作。
 ## 国际秩序与规则
-- **中国是现行国际秩序受益者**：中国在现行国际秩序中发展起来，主张按照大多数国家愿望推动秩序朝着更加公正合理的方向发展。
-- **维护联合国核心地位**：主张共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。
-- **反对双重标准**：在遵守国际法上不能搞双重标准；尊重各国主权和领土完整，就应该支持中国实现完全统一。
+- **中国与国际秩序**：中国是在现行国际秩序中发展起来的，是这一秩序的受益者；中国要做的是按照大多数国家的愿望，推动这一秩序朝着更加公正合理的方向发展，而非另起炉灶。
+- **共同维护规则**：应共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则；只要认同这一点，双重标准就没有存在的空间。
 ## 乌克兰危机
-- **中俄关系定位**：中国同俄罗斯建立不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；中俄交往是正常国与国交往。
-- **中方劝和促谈立场**：2022年2月25日中方即提出对话协商解决；习近平主席提出4点主张——各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。
-- **斡旋行动**：中国派出特使赴各国斡旋，同巴西等南方国家发起“和平之友”。
-- **对和谈进程态度**：中方乐见美国同俄罗斯达成的共识；所有当事方包括利益攸关方都应适时参与和谈进程；欧洲有必要发挥重要作用，共同探讨均衡、有效、可持续的欧洲安全框架。
+- **中俄关系**：中国同俄罗斯是两大邻国，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；中俄交往是正常的国与国之间的交往。
+- **中方立场**：2022年2月25日（危机爆发第2天）中方即提出对话协商解决；习近平主席提出四点主张——各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。
+- **劝和促谈**：中国以此为依据持续推进劝和促谈，派出特使赴各国斡旋，同巴西等南方国家发起“和平之友”；中方乐见一切致力于和平的努力，包括美俄达成的共识，同时认为所有当事方包括利益攸关方都应适时参与和谈进程，欧洲更有必要为此发挥重要作用。
 ## 中美关系
-- **对美政策三原则**：相互尊重、和平共处、合作共赢；中国对美政策保持连续性和稳定性，不会轻易翻烙饼。
-- **中方立场**：中方已准备好按照三原则同美方构建稳定健康可持续的双边关系；若美方仍对中国打压遏制，中方必将奉陪到底，坚决回击美方单边霸凌行径。
+- **对美政策三原则**：中国对美政策保持连续性和稳定性，即习近平主席提出的相互尊重、和平共处、合作共赢三原则；中方愿意按照三原则同美方构建稳定健康可持续的双边关系。
+- **中方立场**：中美制度不同是各自人民做出的选择，想改造或颠覆对方不切实际；若美方仍对中国打压遏制，中国必将奉陪到底，坚定维护国家主权、尊严和正当发展权利，坚决回击美方单边霸凌行径。
 # 官方表态
 ## 多极化主张
-- **平等有序的多极化**：中国给出的答案是推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是对多极世界的真诚期许；中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。
+- **推动平等有序的世界多极化**：中国给出的答案是推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是对多极世界的期许；中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。
 - **倡导平等相待**：坚持权利平等、机会平等、规则平等应成为建设多极世界的基本原则；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权，这不会导致西方的缺失，而将促进世界的正和。
-- **尊重国际法治**：联合国宪章宗旨和原则是国际关系的根本遵循，也是建设多极世界的重要基石；多极格局不能是无序状态，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈；在遵守国际法上不能搞双重标准，要尊重各国主权和领土完整，就应该支持中国实现完全统一。
+- **尊重国际法治**：联合国宪章宗旨和原则是国际关系的根本遵循，也是建设多极世界的重要基石；多极格局不能是无序状态，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈；在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
 - **践行多边主义**：联合国是践行多边主义、推进全球治理的核心平台，未来的多极世界更加需要联合国，对于这座大厦应该固本强基，而不是拆梁毁柱；中国坚持真正的多边主义，倡导共商共建共享的全球治理观。
 - **坚持开放共赢**：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界；保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己；应当坚持开放合作，以普惠包容的经济全球化来支撑平等有序的世界多极化。
-## 国际秩序
-- **中国是现行秩序受益者**：中国是在现行国际秩序中发展起来的，是受益者；要做的不是另起炉灶，而是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向发展。
-- **维护联合国核心地位**：各国应共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数；只要认同这一点，双重标准就没有存在的空间。
-## 乌克兰危机
-- **中俄关系定位**：中国同俄罗斯建立了不结盟、不对抗、不针对第三方的睦邻友好关系，两国交往是正常的国与国之间的交往。
-- **劝和促谈立场**：中国历来主张一切争端和冲突都应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题；从2022年2月25日起中方即提出对话协商解决，习近平主席提出四点主张——各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。
-- **推动和谈进程**：中方派特使斡旋，同巴西等南方国家发起和平之友；乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应适时参与和谈进程；欧洲有必要为此发挥重要作用，共同探讨欧洲的长治久安，找到均衡、有效、可持续的欧洲安全框架。
+## 中欧关系
+- **欧洲是多极世界的重要一极**：中欧双方是伙伴而不是对手；今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作，推动世界走向和平、安全、繁荣、进步的光明前景。
+- **战略对接**：中国愿推动高质量共建"一带一路"，同欧盟的"全球门户"战略相互对接，赋能彼此也赋能世界。
 ## 中美关系
-- **对美政策三原则**：中国对美政策保持连续性和稳定性，不会轻易翻烙饼；对美政策就是习近平主席提出的三原则——相互尊重、和平共处、合作共赢，中方愿意按照三原则同美方构建稳定健康可持续的双边关系。
-- **回应打压的边界**：希望美方相向而行；如果美方仍对中国打压和遏制，中方别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边和霸凌行径。
+- **对美政策三原则**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼；对美政策就是习近平主席提出的三原则——相互尊重、和平共处、合作共赢。
+- **构建稳定健康可持续的双边关系**：中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道；希望美方能够相向而行。
+- **奉陪到底的边界**：如果美方不愿意相向而行，仍对中国打压和遏制，中国别无选择，必将奉陪到底，坚定维护中国的主权、国家的尊严和正当发展权利，坚决回击美方的单边和霸凌行径。
 # Q&amp;A环节
-**主持人**：您提到国际秩序，现在很多人质疑联合国宪章。从俄罗斯入侵乌克兰，到美国总统威胁使用武力入侵格陵兰和巴拿马、以及巴勒斯坦人流离失所，中国也被指责违反海洋法和《世界人权宣言》。您即将前往纽约参加安理会会议，您还相信联合国和联合国宪章吗？是否致力于推动联合国改革？
-**王毅**：你的提问涉及秩序和规则两个关键词。关于秩序，这几年有人说中国要改变秩序、另起炉灶，但现在说这种话的人可能不多了，因为真正挑战秩序、毁约退群的国家出现了。中国是在现行国际秩序中发展起来的，是受益者，我们要按大多数国家的愿望推动秩序朝着更加公正合理的方向发展。关于规则，我们起码应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数。只要认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字和治理赤字，共同构建人类命运共同体。
-**主持人**：2022年慕安会前几天您曾表示任何国家的主权、独立和领土完整都应得到尊重，乌克兰也不例外。如今俄罗斯已成为约翰·麦凯恩所说的"中国的加油站"，中国对乌克兰有很大影响力。在各方施压结束战争的情况下，您能否从中国这边采取措施，比如减少购买俄罗斯油气、降低价格或停止输送军民两用物资，以加大对俄施压？
-**王毅**：中国同俄罗斯是两大邻国，有着漫长边界。两国关系经历过曲折后，我们吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。中俄交往是正常的国与国交往。关于不从俄罗斯买油气，我想问：哪个国家能提供如此巨量的油气满足中国民众需求？那是不可能的，也是不保险的，因为有的国家常把经贸问题政治化、当作打压中国的工具，我们不会允许，要为人民负责。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出四点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。我们派特使斡旋，同巴西等南方国家发起"和平之友"。中方乐见一切致力于和平的努力，包括美俄达成的共识，同时认为所有当事方和利益攸关方都应适时参与和谈进程。这场战事发生在欧洲大地上，欧洲更有必要发挥重要作用，共同探讨欧洲的长治久安，找到均衡、有效、可持续的欧洲安全框架。
-**主持人**：时间已到，能否简要预告您认为中美关系将如何发展？
-**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不同是各自人民的选择，想改造或颠覆对方不切实际，正确态度是相互尊重，这是中美交往的前提；和平共处理所当然，中美两个大国总不能冲突起来，因为那将殃及整个世界，所以要开展对话、加强交往、增进了解、建立信任；合作共赢是因为国际社会期待中美合作，全球性挑战也需要中美携手应对。中方已准备好，愿意按照三原则同美方构建稳定健康可持续的双边关系。我们希望美方相向而行，但如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚定维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼，新中国就是在战胜各种艰难险阻中发展壮大起来的。我们对世界前途和中美关系未来都充满信心，中美共同努力的方向就是相互尊重、和平共处、合作共赢。</t>
+**主持人**：您提到国际秩序，我开场也强调要尊重联合国宪章，但现在看到很多质疑——俄罗斯入侵乌克兰、美国总统威胁对格陵兰和巴拿马动武、巴勒斯坦人流离失所，中国也被指责违反海洋法和《世界人权宣言》。您接下来要去纽约参加安理会会议，您还相信联合国和宪章吗？会推动联合国改革吗？这有多优先？
+**王毅**：你的提问涉及秩序和规则两个关键词。关于秩序，这几年有人说中国要改变秩序、另起炉灶，但现在真正挑战秩序、毁约退群的国家出现了，欧洲朋友们可能每天都在感受寒意。中国是在现行国际秩序中发展起来的，是受益者，我们要按大多数国家愿望推动秩序朝更加公正合理方向发展。关于规则，我们应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。只要认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议和构建人类命运共同体理念，希望各国超越历史文化社会制度意识形态不同，共同呵护人类唯一可居住的星球。
+**主持人**：2022年慕安会前几天您说过，任何国家的主权、独立和领土完整都应得到尊重和保障，乌克兰也不例外。现在俄罗斯已成为约翰·麦凯恩所说的"中国的加油站"，我补充说是有军队的加油站。您能否利用对乌克兰的影响力，比如减少从俄罗斯购买天然气、降低价格或停止双用途货物，加大对俄压力以结束战争？
+**王毅**：中国同俄罗斯是两大邻国，有着漫长边界，两国关系经历过曲折后吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。中俄交往是正常的国与国交往。关于不从俄罗斯买油气，我想问哪个国家能提供如此巨量油气满足中国民众需求？那不可能也不保险，因为常有国家把经贸问题政治化、当作打压中国工具，我们不会允许，要为人民负责。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。乌克兰危机爆发第二天即2022年2月25日，中方就提出对话协商解决。习近平主席提出四点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。我们以此推进劝和促谈，派特使斡旋，同巴西等南方国家发起和平之友。中国立场是公正客观、理性务实的，体现国际社会最大共识。任何冲突终点都是谈判桌，中方乐见一切致力于和平的努力，包括美俄达成的共识，同时认为所有当事方和利益攸关方都应适时参与和谈。战事发生在欧洲大地，欧洲更有必要发挥重要作用，共同探讨欧洲长治久安，找到均衡有效可持续的欧洲安全框架。
+**主持人**：时间快到了，请您简短预告一下中美关系将如何发展。
+**王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不一样，是各自人民的选择，想改造或颠覆对方不切实际，正确态度是相互尊重，这是中美交往前提。和平共处理所当然，中美两个大国总不能冲突起来，那将殃及整个世界，所以要开展对话、加强交往、增进了解、建立信任。合作共赢是因为国际社会期待中美合作，全球性挑战需要中美携手应对，这也是两个大国应承担的国际责任。中方已准备好按三原则同美方构建稳定健康可持续的双边关系，希望美方相向而行。如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚定维护中国主权、国家尊严和正当发展权利，坚决回击美方单边霸凌行径。中国人从来不信邪、不怕鬼，新中国就是在战胜各种艰难险阻中发展壮大起来的。我们对世界前途和中美关系未来都充满信心，中美只有一个共同努力方向，就是相互尊重、和平共处、合作共赢，这也是国际社会最大期待。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>43</v>
+        <v>45.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/4097</t>
+          <t>7004/4386</t>
         </is>
       </c>
     </row>
@@ -785,94 +784,83 @@
       <c r="C3" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-电子科技大学电子科学与工程学院面向考生及家长举办招生宣讲会，由学院段院、柳教授、张教授、李天明教授及在读博士生田雨桐分别介绍学院整体情况与各学科方向，旨在帮助考生和家长了解学院学科实力、师资科研与人才培养情况，吸引优秀生源报考。整体宣讲以学院历史沿革、学科方向、科研平台、师资队伍及学生发展为主线，辅以在校生视角的择校建议，并现场解答了关于夏令营安排等招生咨询问题，整体基调为积极推介与开放答疑。
+电子科技大学电子科学与工程学院面向考生和家长举办招生宣讲会，由学院段院、柳教授、张教授、李天明教授及在读博士生田雨桐作为分享嘉宾，围绕学院整体情况、电子信息材料与元器件、电磁场与微波技术与电路与系统、物理电子学等学科方向以及学生视角的就读体验进行介绍，旨在帮助考生和家长全面了解学院实力与培养特色，吸引优秀生源报考。宣讲过程中，嘉宾还就观众关心的夏令营安排进行了解答，明确学院计划今年举办夏令营但具体时间待定，相关信息将通过学院QQ群发布，整体宣讲氛围积极，互动顺畅。
 # 核心信息与数据
 ## 学院整体情况
-- **历史沿革**：1956年建校时成立无线电系、电真空器件系、无线电零件系，经1979年、1992年、2001年、2018年4次院系调整，成立电子科学与工程学院（科普示范性微电子学院）；2023年响应国家号召，成立电子科学与工程学院与基层电路学院（原文如此）。
-- **学科设置**：电子科学与技术为国家重点一级学科，下设5个二级学科方向——电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构（原文如此）。
-- **国防特色学科**：电磁场与微波军用关键材料、电子元器件（原文如此）。
+- **历史沿革**：1956年建校之初成立无线电系、电真空器件系、无线电零件系；1979年、1992年、2001年、2018年经4次院系调整成立电子科学与工程学院（科普示范性微电子学院）；2023年响应国家号召成立电子科学与工程学院与基层电路学院。
+- **学科设置**：电子科学与技术为国家重点一级学科，下设5个二级学科方向——电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构；另有3个国防特色学科——电磁场与微波军用关键材料、电子元器件。
 - **党建荣誉**：学校党委入选教育部首批全国党建工作标杆院系学院，学院荣获全国教育系统先进集体。
-- **本科生规模**：现有本科生1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业、国家级一流本科专业建设点）与电磁场与无线技术两个专业方向。
-- **研究生规模**：现有硕士和博士研究生1975人，招生专业为学术型博士/硕士电子科学与技术、材料科学与工程，专业学位博士/硕士电子信息、材料工程。
-- **师资构成**：现有教师302人，其中教研系139人、科研系95人、教学系14人、实验系21人，教师总数269人，机关33人。
-- **高层次人才**：两院院士2人、领军人才19人、青年人才28人、其他类型人才12人、后继61人（原文如此）。
-- **教师团队**：融合两个全国高校黄大年式教师团队，2022年融合4个国家自然科学基金创新群体。
-- **科研经费**：近5年科研经费到账稳定在3—4亿元之间，项目构成以纵向项目为主、横向项目为辅。
-- **科研成果**：牵头获得国家科技奖励11项；近5年发表高水平学术论文2000余篇；专利申请1600余件、授权1300余件。
-- **科研团队**：共20个科研团队，年度经费过千万元的团队15个，其中过亿元团队1个。
-- **科研平台**：拥有国家电子辐射控制材料工程技术研究中心、微波电子工器件国家级重点实验室（原文如此）两个国家级平台，4个国际合作平台，7个省部级科研平台。
-- **国际交流**：共建国际姊妹院系两个——香港大学电机工程电子系、香港城市大学电子工程系；主办高水平国际会议13场；学生长短期交流项目20多个。
+- **本科生培养**：现有本科生1545人，招生专业为工科试验班（电子工程类），含两个专业方向——电子科学与技术（国家特色专业、国家级一流本科专业建设点）、电磁场与无线技术。
+- **研究生培养**：现有硕士和博士研究生1975人；学术型博士/硕士招生专业为电子科学与技术、材料科学与工程；专业学位博士/硕士招生专业为电子信息、材料工程。
+- **师资队伍**：现有教师302人，其中教研系列139人、科研系列95人、教学系列14人、实验系列21人、机关33人；两院院士2人、领军人才19人、青年人才28人、其他类型人才12人。
+- **科研经费与成果**：近5年科研经费到账稳定在3–4亿元之间，以纵向项目为主、横向项目为辅；牵头获国家科技奖励11项；近5年发表高水平学术论文2000余篇；申请专利1600余件、授权1300余件。
+- **科研团队与平台**：共20个科研团队，年度经费过千万元的团队15个，其中过亿元团队1个；拥有2个国家级平台——国家电子辐射控制材料工程技术研究中心、微波电子工器件国家级重点实验室（原文如此），4个国际合作平台、7个省部级科研平台。
+- **国际交流**：共建国际姊妹院系2个——香港大学电机工程电子系、香港城市大学电子工程系；主办高水平国际会议13场，学生长短期交流项目20多个。
 ## 电子信息材料与元器件方向
-- **方向内涵**：以材料为基础、器件为核心、应用为目标导向，涉及电子材料与电子器件的设计、研制、生产与应用，涵盖电磁、声、光、热、力及化学生物等特性。
-- **产业背景**：2021年中国集成电路电子产品进口额度达2.8万亿元，约为原有进口量的1.7倍；先进电子材料元器件电路系统等电子产品是我国目前最为紧迫的卡脖子问题之一。
-- **应用领域**：在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域起重要作用，已广泛应用于物联网、移动设备、网络基础设施、无人驾驶、航空航天、医疗健康和可穿戴设备，达到万亿美元量级。
-- **发展趋势**：电子产品向小型化、多功能、低功耗、智能化方向发展，元器件朝微型化、片式化、集成化、薄膜化和智能化发展，强调材料和器件一体化；集成技术将摩尔定律制程缩小与超摩尔定律功能多样化相结合。
-- **邓龙江院士团队**：电磁辐射控制材料与技术团队，现有研究人员19人（正高13人、副高15人），近年发表包括《自然》在内的论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步或技术发明二等奖共计3项。
-- **张怀武教授团队**：磁电薄膜与微型器件团队，现有研究人员17人（正高15人、副高2人），开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目等100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
-- **国家电磁辐射控制材料工程技术研究中心**：历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级形成国家级平台，开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地。
-- **电磁薄膜与集成器件全国重点实验室**：2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建，围绕电子信息系统微小型化和单片集成的重大需求开展研究，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向。
-- **研究条件**：科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，拥有大型设备或系统500余台套；材料制备设备约50台套，微纳加工设备30台套，微观表征设备10余台套，性能测试设备50余台套。
-- **方向成果**：已获国家科技技术发明等奖项共计7项，在《自然》及子刊每年有多篇重要文章发表。
-- **毕业生去向**：遍布产业界与学术界，包括英特尔、中芯国际、华为、德州仪器及高校科研院所。
-- **学生代表成果**：在读学生杨伟豪以第一作者在《自然·电子》《自然·通讯》各发表一篇论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；黄飞获2018年四川省优秀毕业生并获斯坦福大学攻读博士全额奖学金；李凤霞读博期间发表论文16篇（一作6篇）；严巍获21届王大珩光学奖，以优秀青年学者身份加入苏州大学；毕业生万位现任河北美泰电子科技公司副总，带领团队采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
-## 电磁场与微波技术和电路与系统方向
-- **电磁场与微波技术细分方向**：包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向。
-- **电路与系统细分方向**：包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
-- **学科历史**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生共同创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业；所属一级学科电子科学与技术入选双一流A类学科。
-- **研究团队**：电磁场与微波技术学科由6个团队组成——电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
-- **学科平台**：包含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心及国家级重点实验室；硬件方面拥有中国高校最为先进的微波暗室群体及微波毫米波太赫兹仿真测试平台。
-- **天线方向成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能；强耦合超宽带相控阵成果应用于中电14所某大型机载相控阵雷达；樊勇教授团队研究毫米波平面集成天线，可应用于毫米波通信雷达系统。
-- **测量与电磁兼容成果**：李恩教授团队微波毫米波测量技术突破众多技术封锁，有60多年技术积累；杨世文教授团队电磁测井仪器获国家科技进步二等奖1项，成果在中海油推广应用。
-- **微波毫米波电路成果**：延波教授团队（原文如此）引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委项目支持，应用于新一代高速通信系统；在固态合成功率源、天线阵列、扩电网络（原文如此）等电路与通信雷达系统及三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端等微系统技术方面取得进展。
-- **计算电磁学与太赫兹成果**：杨世文教授团队计算电磁学相关算法被评为20世纪十大算法之一；樊勇教授团队成功研制0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米；太赫兹通信成果在2023年成都大运会田径项目成功示范应用。
-- **电磁波应用成果**：李恩教授团队面向5G通信、高性能系统、生物医学、新能源等方向开展电磁波与物质互作用机理及测评系统研究；生物医学电磁学及成像方向发表大量高水平论文，有20余项国家发明专利。
-- **电路与系统学科沿革**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站；学科包含教育部国际合作联合实验室及国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
-- **电路与系统研究成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制；樊勇教授和张静直（即张教授本人）团队从事毫米波通信雷达CMOS芯片研究；康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统、雷达系统研制成果。
-- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，荣获华为优秀合作项目奖、研究生优秀导学团队提名奖；学生获互联网+奖项、国际HPV（原文如此）各类奖项及优秀论文、创新创业大赛奖项。
-- **就业方向**：就业领域分布广泛，包括华为、中兴等行业领军企业及各大研究所、高校，毕业生在海外留学方面也取得突破。
+- **方向内涵**：以材料为基础、器件为核心、应用为目标导向，涉及电子材料、器件、电路的设计研制生产与应用；以电子在物质中的输运特性（电磁声光热力、化学生物类比特性）及外部作用为基础。
+- **产业背景**：2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍；先进电子材料元器件电路系统等电子产品是我国目前最为紧迫的卡脖子问题之一。
+- **应用领域**：电子产品在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域起重要作用，广泛用于物联网、移动设备、网络基础设施、无人驾驶、航空航天、医疗健康和可穿戴设备，市场规模达万亿美元量级。
+- **发展趋势**：元器件朝微型化、片式化、集成化、薄膜化、智能化方向发展，强调材料和器件一体化；集成技术将摩尔定律制程缩小与超摩尔定律功能多样化相结合。
+- **邓龙江院士团队**：电磁辐射控制材料与技术团队，现有研究人员19人（正高13人、副高15人）；近年发表包括自然（原文如此）在内的论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步或技术发明二等奖共计3项。
+- **张怀武教授团队**：磁电薄膜与微型器件团队，现有研究人员17人（正高15人、副高2人）；重点开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究；承担国家重点研发计划、自然基金重点重大科学仪器项目、国际合作等项目100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
+- **国家级平台一**：国家电磁辐射控制材料工程技术研究中心，历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级形成；主要开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地。
+- **国家级平台二**：电磁薄膜与集成器件全国重点实验室，2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建；围绕电子信息系统微小型化和单片集成的重大需求，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向。
+- **研究条件**：科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备或系统500余台套；材料制备设备约50台套，微纳加工设备30台套，微观表征设备10余台套，性能测试设备50余台套。
+- **研究成果与毕业生**：已获国家技术发明等奖项共计7项；毕业生遍布英特尔、中芯国际、华为、德州仪器及高校科研院所；在读学生杨伟豪以第一作者在自然电子、自然通讯各发表论文1篇；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖。
+## 电磁场与微波技术、电路与系统方向
+- **电磁场与微波技术细分方向**：包含4个细分方向——微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术，涵盖射频微波整套系统全部研发方向。
+- **电路与系统细分方向**：包含3个方向——非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统。
+- **学科历史**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生共同创建；形成电磁场与无线技术国家特色专业及电波传播与天线国防紧缺特色专业；所属一级学科电子科学与技术入选双一流A类学科。
+- **科研团队**：电磁场与微波技术方向由6个团队组成——电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
+- **学科平台**：包含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心及国家级重点实验室；硬件方面拥有中国高校最为先进的微波暗室群体及微波毫米波太Hz仿真测试平台。
+- **天线方向成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能；相关成果应用于中电14所某大型机载相控阵雷达；樊勇教授团队研究毫米波平面集成天线，可应用于毫米波通信雷达系统。
+- **测量与电磁兼容成果**：李恩教授团队引领微波毫米波测量技术，突破众多技术封锁，有60多年技术积累；杨世文教授团队在电磁测井仪器方面获国家科技进步二等奖一项，成果在中海油成功推广应用。
+- **微波毫米波电路成果**：延波教授团队引领微波毫米波太Hz芯片研究，获国家科技重大专项及军科委项目支持，应用于新一代高速通信系统；在固态合成功率源、天线阵列、扩电网络等电路与通信雷达系统及三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端等微系统技术方面取得进展。
+- **计算电磁学与太Hz成果**：杨世文教授团队计算电磁学相关算法被评为20世纪十大算法之一；樊勇教授团队成功研制0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米；太Hz通信技术成果在2023年成都大运会田径项目成功示范应用。
+- **电磁波应用成果**：李恩教授团队面向5G通信、高性能系统、生物医学、新能源等方向提供电磁波与物质互作用机理及测评系统研究成果；在生物医学电磁学及成像方向发表大量高水平论文，获20余项国家发明专利。
+- **电路与系统学科概况**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站；包含教育部国际合作联合实验室及国家高等学校学科创新引智基地；拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
+- **电路与系统研究成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制；樊勇教授和张教授（本人）团队工作在毫米波通信雷达CMOS芯片方向；康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统、雷达系统研制成果。
+- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，荣获华为优秀合作项目奖、研究生优秀导学团队提名奖；学生获互联网+奖项、国际HPV（原文如此）各类奖项及优秀论文、创新创业大赛奖项；就业领域包括华为、中兴等行业领军企业及各大研究所、高校。
 ## 物理电子学方向
-- **学科定义**：物理电子学是物理学与电子科学技术的交叉学科，将物理学最新研究成果应用于电子学中产生新电子器件；典型应用包括微波电子学（微波电真空器件）和光电子学（光电器件）。
-- **学科特点**：内容不断充实（如量子电子学内容逐渐增加）；学科边界不一定清晰，如光电子学既可属物理电子学也可属光学工程一级学科；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
-- **学校发展历程**：起源于1956年建校时在前苏联专家帮助下成立的电子控器件专业（原文如此），归属电子器件系；1979年在刘成刚院士（原文如此）带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年物理电子学院、电工学院和微工学院部分成立现在的电子科学与工程学院。
-- **纵向发展**：上游为仿真设计（拥有自主知识产权商用软件MMST和切皮克，原文如此），并引入人工智能方向到器件设计和电子学应用；下游为系统应用，包括用回旋行波管研制毫米波雷达、用行波管做无线输能系统、用磁控管做微波能干燥系统。
-- **横向发展**：频段从微波上移至毫米波到太赫兹；与医学交叉，利用太赫兹分辨率高、透视效果好的特点做太赫兹成像用于医学诊断，利用太赫兹宽频带特点做保密通信和高速通信。
-- **科研平台与经费**：有三个四川省工程中心或重点实验室，参与成立一系列行业协会；每年到校科研经费接近2亿元，在学院中最多；2023年成功举办行业顶级会议；物理电子学方向共有9个团队。
-- **国际地位**：是国际上最大的真空器件研究中心（原文如此），在国际上名气越来越大。
-- **学生出口**：李天明教授团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；李天明教授个人每年约两个硕士毕业、一个博士毕业。
+- **学科定义**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学中产生新电子器件；典型应用包括微波与电子相互作用形成微波电子学（微波电真空器件）、光与电子相互作用形成光电子学（光电器件）。
+- **学科特点**：内容不断充实（如量子电子学内容逐渐增加）；学科边界不一定清晰（如光电子学既可属物理电子学也可属光学工程一级学科）；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
+- **学校发展历程**：1956年建校时在前苏联专家帮助下成立电子控器件专业，归属电子器件系；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年物理电子学院、电工学院和微工学院部分成立现在的电子科学与工程学院。
+- **纵向发展**：上游为仿真设计数字模拟材料，拥有自主知识产权商用软件MMST和切皮克（原文如此），并将人工智能引入器件设计和电子学应用；下游为系统应用，包括毫米波雷达（回旋行波管）、无线输能系统（行波管）、微波能干燥系统（磁控管）。
+- **横向拓展**：频段从微波上移至毫米波到太赫兹；与医学交叉，利用太赫兹分辨率高、透视效果好的特点做太赫兹成像用于医学诊断，利用太赫兹宽频带特点做保密通信和高速通信。
+- **科研平台与经费**：拥有3个四川省工程中心或重点实验室，参与成立一系列行业协会；每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心；2023年成功举办行业顶级会议。
+- **团队与学生出口**：物理电子学方向共有9个团队；团队学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；李天明教授个人每年约两个研究生毕业、一个博士毕业。
 ## 学生视角分享
 - **城市优势**：成都是四川省会、国家中心城市、新一线城市、国家历史文化名城、古蜀文明发祥地、中国十大古都之一；电子信息产业发达，英特尔、华为、京东方等巨头汇聚，提供实践平台和就业资源。
-- **学校优势**：电子科技大学是我国电子信息人才培育的代名词，拥有电子信息博物馆，记录我国第一台晶体管收音机的诞生；从电子科学与技术、信息与通信工程到集成电路科学与技术，构建了最完整的电子信息学科群。
-- **学科实力**：电子科学与技术学科在第4轮学科评估中斩获A+，稳居全国第一；学院拥有四大学科和19个科研团队。
-- **团队情况**：田雨桐所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，覆盖从芯片、封装、天线、电路、模块到系统的全面知识。
-- **就业情况**：团队硕博毕业生实现100%就业率，就业单位有各类民营企业、大型央国企和头部科研院所。
-- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金及校园地国家助学贷款和生源地助学贷款。
-- **择校建议**：先根据研究方向选择研究团队，再选择合适导师；可通过学院网站进入团队网页找导师，也可借助IEEE和中国知网等文献检索网站检索导师论文和指导研究生毕业情况。
+- **学校实力**：电子科技大学是我国电子信息人才培育的代名词，拥有电子信息博物馆，记录我国第一台晶体管收音机的诞生；从电子科学与技术、信息与通信工程到集成电路科学与技术，构建了最完整的电子信息学科群。
+- **学科评估**：学院电子科学与技术学科在第4轮学科评估中斩获A+，稳居全国第一；从电磁场与微波技术到微电子与固体电子学，五大国防特色学科构建了深厚学科底蕴。
+- **团队选择**：学院拥有四大学科和19个科研团队；田雨桐所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，硕博毕业生就业率100%。
+- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金及校园地国家助学贷款、生源地助学贷款。
+- **择校建议**：先按研究方向选择研究团队，再选择导师；可通过学院网站了解团队，借助IEEE、中国知网等文献检索网站检索导师论文和指导研究生毕业情况，提前沟通交流。
 # 各方立场与诉求
-- **主持人（发言者1）**：关注考生和家长关心的夏令营安排，在直播中提问夏令营有无具体时间和形式。
-- **段院**：回应称电子学院计划今年举办夏令营活动，但具体时间待定，建议感兴趣的同学加入学院QQ群，相关信息将及时发布。
-- **主持人（发言者1）**：补充公布学院QQ群号978499108，邀请考生和家长入群咨询了解。
-- **考生和家长（弹幕区）**：通过弹幕提出夏令营相关问题，主持人收集后转达给学院老师解答。
-- **段院、柳教授、张教授、李天明教授**：分别介绍学院整体情况、电子信息材料与元器件、电磁场与微波技术和电路与系统、物理电子学等学科方向，面向考生和家长进行招生宣传。
-- **田雨桐（在读博士生）**：从学生视角分享选择电子学院的8个理由及择校择专业建议，回应考生和家长关心的就业、奖助体系、导师选择等问题。
+- **主持人（发言者1）**：代表考生和家长提出夏令营具体时间与形式的咨询，并引导观众通过弹幕提问。
+- **段院（发言者2）**：回应夏令营问题，表示学院计划今年举办夏令营活动，具体时间待定，建议考生加入学院QQ群（978499108）获取后续信息。
+- **柳教授（发言者3）**：介绍电子信息材料与元器件方向，强调该方向以材料为基础、器件为核心、应用为目标导向，指出先进电子材料元器件电路系统等是我国目前最为紧迫的卡脖子问题之一，并展示团队实力与毕业生去向。
+- **张教授（发言者4）**：介绍电磁场与微波技术、电路与系统两个专业方向，说明学科历史沿革、团队构成、科研成果及人才培养情况，并表达欢迎考生报考的意愿。
+- **李天明教授（发言者5）**：介绍物理电子学学科定义、学校发展历程、研究拓展方向及学生出口情况，强调该方向每年科研经费接近2亿元，为学院最多，是国际上最大的真空器件研究中心。
+- **田雨桐（博士研究生）**：从学生视角分享选择电子学院的8个理由，包括城市优势、学科实力、团队资源、奖助体系等，并给出择校和选导师建议，鼓励考生报考。
 # 达成共识
-- **夏令营安排**：段院明确回应，电子学院**计划今年举办夏令营活动**，具体时间待定，相关信息将通过学院QQ群及时发布。
-- **咨询渠道**：学院公布招生咨询QQ群号 **978499108**，考生和家长可扫码或搜索群号加入，进行详细咨询和了解。
-- **直播抽奖**：本场直播抽奖口令为「一生一世，逐梦未来」，中奖同学需私信后台留下联系方式和收货地址，奖品为学校定制马克杯一套。
+- **夏令营安排**：电子学院计划今年举办夏令营活动，具体时间待定，相关信息将通过学院QQ群（978499108）及时发布。
+- **招生口径**：学院欢迎考生和家长通过QQ群进行详细咨询和了解，后续夏令营及研究生入学相关安排将通过该渠道通知。
 # 待协调事项与后续
 ## 待协调事项
-- **夏令营活动**：电子学院计划今年举办，具体时间待定，相关信息将通过学院QQ群发布
+- **夏令营活动**：电子学院计划今年举办，具体时间与形式待定，段院负责，相关信息将通过学院QQ群发布
 ## 后续安排与参与方式
-- **学院招生咨询QQ群**：978499108，考生和家长可扫码或搜索群号加入，咨询夏令营及招生相关问题
-- **夏令营信息发布**：时间确定后将在QQ群内及时发布，感兴趣的同学可关注群消息
-- **直播抽奖**：中奖同学（发现、小提琴、小镇里的人、4830、魏军老同学等）可私信后台留下联系方式和收货地址，奖品为电子科技大学定制马克杯一套（含勺子和杯盖）</t>
+- **学院QQ群**：978499108，考生和家长可扫码或搜索群号加入，咨询夏令营及报考相关问题
+- **夏令营信息发布**：时间确定后将在QQ群内及时发布，感兴趣的同学需关注群消息
+- **直播抽奖**：口令为「E生一世，逐梦未来」，中奖同学需私信后台留下联系方式和收货地址，奖品为电子科技大学马克杯套装（含勺子和杯盖）</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/6228</t>
+          <t>13887/5922</t>
         </is>
       </c>
     </row>
@@ -1409,154 +1397,171 @@
       <c r="C4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次复盘会为公司2023年度总结与年终奖颁发会议，由老板主持，围绕年度经营数据、年终奖发放标准、员工评价与部门总结、颁奖及抽奖等环节展开。预期目标为总结2023年公司发展状况、公布年终奖、评价员工并颁发奖项、展望2024年。实际结果方面，老板公布年终奖总额226,000元，成本支出390万元，利润率约24%或27%，最高工资（含年终奖）有2-3人达20万元以上，平均到手工资约1万多元；2023年平时工资总额提高约25万元，年终奖比去年多13万多元，干满一年的员工从去年的4-5人增至12人，公司尚有百来万未收回款项。老板指出成本控制是最大问题，根源在于老板管理不足，并承认对员工关心不够、不够雷厉风行。会议逐一评价员工并颁发最佳新人奖、最佳进步奖、后期独挡一面奖、最佳员工奖、特别贡献奖五项奖项，各部门总结2023年工作并展望2024年，最后进行抽奖并宣布当日报销福利。
+2023年度总结与年终奖颁发大会于年末召开，老板主持，围绕经营数据公布、年终奖发放、员工与部门评价、颁奖及抽奖等环节展开。预期目标为总结年度发展、兑现员工激励并明确来年方向；实际结果方面，公司全年总量提升，年终奖总额226,000元，成本支出390万元，利润率约24%或27%，最高工资（含年终奖）有2-3人达20万元以上，平均工资到手约1万多元，干满一年员工由去年4-5人增至12人。老板指出成本控制差、有百来万未收回、结余缩水，但总量提升是能发奖的根本原因。会议逐一点评员工并颁发最佳新人、最佳进步、后期独挡一面、最佳员工、特别贡献五项奖，对短视频、执行、商务三部门作评价与展望，明确短视频部门明年开始变现、商务部门实打实项目约300万元等目标，并承认对部门支持与管理关心不够，成本控制、加班人员不足等问题留待明年再议。
 # 结果与关键成果
 ## 交付与里程碑
-- **年度经营数据公布**：2023年年终奖总额为226,000元，个人数额不逐一公布；成本支出（人员工资、外援配音、字幕、租机器等）为390万元，利润率约24%或27%。
-- **员工收入提升**：最高工资（含年终奖）有2-3人达到20万元以上，平均到手工资约1万多元；平时工资总额提高约25万元，年终奖比去年多13万多元。
-- **人员留存改善**：干满一年的员工从去年的4-5人增加到今年的12人。
-- **短视频账号增长**：视频号粉丝从3月1日的700人增长到8万，小红书从2000+增长到6.4万，抖音从2000+增长到5.7万，B站从3.1万增长到7.6万；增长转折点为6月20日第一条外出拍摄对话视频。
-- **账号变现进度**：课程变现评分达7.5分（满分10分），其中0.5分为期待空间；重点项目变现未完成。
-- **直播开展情况**：视频号直播4-5场，平均在线人数每场5000人以上，前100人平均在线50分钟以上。
-- **商务部门业绩**：实打实项目约300万元，基本达到预期。
-- **颁奖仪式**：共设5项奖项、6人获奖，包括最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李不续）、最佳员工奖（游腾宇）、特别贡献奖（李海腾）；证书为皮质定制，每本40元含设计费，另有两个洗手包（价值七八十元）未寄到。
-- **抽奖与福利**：抽奖奖品包括充电宝（约79元）、观影券（30元）、洗头膏（七八十元），老板另设100元红包奖；当天看电影或吃饭在一定额度内可报销，仅限当天。
+- **2023年度总结会**：老板公布全年经营数据、年终奖总额与发放标准，逐一点评员工并颁发5项奖项，对短视频、执行、商务三个部门进行评价与展望，最后组织抽奖。
+- **短视频账号运营**：2023年3月1日至年底，视频号粉丝从719人增至8万；小红书从2000+增至6.4万；抖音从2000+增至5.7万；B站从3.1万增至7.6万。涨粉转折点为6月20日第一条外出拍摄对话视频。
+- **账号变现进度**：课程变现按十分制自评达到7.05分（含0.5分期待空间），重点项目变现目标未完成；视频号直播4-5场，平均每场在线人数5000+，前100人平均在线时长50分钟以上，因暂无课程尚未实现直播变现。
+- **商务部门业绩**：2023年实打实承接项目约300万元（含入围等未签约项目则更多），基本达到预期。
+- **颁奖环节**：共6人5项奖——最佳新人奖颁给红叶子、张扬；最佳进步奖颁给欧阳小元；后期独挡一面奖颁给李不续；最佳员工奖颁给游腾宇；特别贡献奖颁给李海涛（奖金为单项奖中最多）。评奖标准为2选1或3选1，有竞争性。
+- **抽奖与福利**：共15个奖品，含一等奖充电宝（约79元）、二等奖观影券（30元）、三等奖洗头膏（约七八十元），另设100元红包奖；当日看电影或吃饭在额度内可报销，但来年不一起聚餐；林彦腾在群里发200元红包。
 ## 数据与指标
-- **年终奖总额**：226,000元。
-- **成本支出**：390万元（含人员工资、外援配音、字幕、租机器）。
-- **利润率**：约24%或27%，老板评价为"非常不可观"。
-- **最高收入**：2-3人含年终奖到手达20万元以上。
-- **平均工资**：到手1万多元。
-- **未收回款项**：百来万元，公司结余到账有所缩水。
-  - 视频号：700人（3月1日）→ 8万
-  - 小红书：2000+（1月）→ 6.4万
-  - 抖音：2000+ → 5.7万
-  - B站：3.1万 → 7.6万
-- **直播数据**：4-5场，平均在线5000人+/场，前100人平均在线50分钟以上。
-- **商务部门项目额**：实打实约300万元。
+- **年终奖总额**：2023年年终奖转账总额为226,000元。
+- **成本支出**：人员工资、外援配音、字幕、租机器等实打实支出390万元。
+- **利润率**：约24%或27%，老板评价"非常不可观"。
+- **员工收入**：最高工资（含年终奖）有2-3人到手达20万元以上；平均工资到手约1万多元。
+- **人工支出变化**：2023年平时工资总额比去年提高约25万元；年终奖比去年多13.12万元。
+- **人员稳定性**：干满一年的员工从去年的4-5人增加到今年的12人。
+- **公司结余**：总量提升但成本上升，到账结余往下跑，另有百来万未收回，结余稍缩水。
+## 制度与流程
+- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元，今年约1000元；干满一年以一个月基本工资为基准，表现好可更高；超过一年主要看当年表现，不再过多考虑年限；干得久且非常满意，预算可达大几万。
+- **个人年终奖不逐一公布**：老板明确个人数额不一一公布，以发到手为准。
+- **评奖机制**：奖项评选为2选1或3选1，有竞争性；未获奖不代表能力不行，但证明该项不突出。
+- **颁奖侧重说明**：老板明确年终奖与奖项对后期执行部门有所侧重，是唯一愿意解释的发放原因。
+- **加班补贴**：年终奖中考虑加班因素，额外补贴约一两千元。
+- **报销福利**：当日看电影或吃饭在额度内可报销，但来年不一起聚餐。
 ## 团队与人员
 ### 红叶子
-- **综合评价**：入职两三个月（10月入职，11月转正），政委给予非常高评价，称"很难招到这样的一个人才，既懂技术又懂英语，而且有把事情做好的精神头"。
-- **工作态度**：在工资表意见栏会写如何把项目做得更好的建议，认真对待工作。
-- **奖项**：获最佳新人奖。
+- **综合评价**：入职两三个月（10月入职，11月转正），政委给予非常高评价，称"很难招到这样的一个人才"。
+- **能力**：既懂技术又懂英语，有把事情做好的精神头；在工资表意见栏会认真写如何把项目做得更好的建议。
 ### 郭东辉
-- **运营能力**：非常有经验的运营，克服了本不应面对的困难，包括达人对接方面受限。
-- **账号运营成果**：负责多平台运营，6月20日说服潘老师外出拍摄后各平台粉丝大幅增长；在6月20日前潘老师曾10次提醒其"出去找工作"，郭东辉坚持未放弃。
-- **工作负荷**：一人负责多个平台运营（正常情况下一个平台一人负责），后红叶子加入负责剪辑及课程上架、开店等事务。
-- **工作方法**：所有内容与直播决策有数据支撑，每晚8-9点抽一小时刷英语老师直播间学习。
-- **自我评价**：最大收获是认知上"说服自己最难"，最大敌人是自己；6月前处于混日子状态，无收获感、成就感、幸福感，后认识到"混日子比充实的日子更痛苦"。
+- **综合评价**：干满一年的运营，非常有经验，克服了本不应面对的一些困难。
+- **限制因素**：老板承认公司限制了他的发挥，应表示歉意。
+- **账号运营成果**：负责多平台运营，2023年各平台粉丝数大幅增长，从6月20日外出拍摄视频开始转变；在6月20日前潘老师曾10次提醒其出去找工作，郭东辉坚持不放弃，说服潘老师外出拍摄后项目出现起色。
 ### 游腾宇
-- **职业性**：对老板和客户回复都非常专业，沟通能力强，"他说的就是我说的，比我说的还行"。
-- **纪律性**：几乎没有迟到，请假严格按规定提前告知并安排工作。
-- **技术能力**：反馈好，客户（宁波城市罗峰）向政委反馈"如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了"；重要活安排给游腾宇后老板"把这个活忘了，肯定不会有任何问题"。
-- **效率**：效率最高且不出问题，做得好。
-- **年终奖**：刚满一年但给老板"干了5、6年老员工"的错觉，因林海腾肯定在既定标准上再拉一档，年终奖"可能还会翻倍"。
-- **奖项**：获最佳员工奖（含金量最高，奖金稍多）。
+- **综合评价**：老板评价最高，"没有之一"，职业性、专业性、纪律性最好。
+- **职业性**：对老板和客户回复都非常专业，沟通能力强，老板称"他说的就是我说的，比我说的还行"。
+- **纪律性**：几乎没有迟到，请假严格按规定提前告知并安排好工作。
+- **技术反馈**：宁波城市项目客户罗峰向政委反馈"如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了"；重要活老板会问林远腾安排给谁，若安排给游腾宇则完全放心。
+- **年终奖**：因林海腾肯定，在既定标准上再拉一档；刚满一年但给老板"干了5、6年老员工"的错觉，年终奖会翻倍。
 ### 欧阳小元
-- **工作态度**：认真，技术水平有学习能力，进步明显。
+- **综合评价**：刚满一年，有认真的工作态度和较强的学习能力，技术水平有进步。
 - **提升空间**：沟通能力需再爬坡。
-- **奖项**：获最佳进步奖，技术进步"明显跑了一截"。
+- **奖项**：获最佳进步奖，技术进步"明显的跑了一截"。
 ### 徐艺玲
-- **工作质量**：一遍过的非常多，仔细认真，"挑不出什么毛病"。
-- **技术进步**：原先只能剪课程，今年剪宣传片类"像模像样"。
-- **项目表现**：杨晶项目中其他人做不了，客户点名"还是让那个小姑娘来做"。
+- **综合评价**：干得较久的员工，一遍过率非常高，工作仔细认真，"挑不出什么毛病"。
+- **技术提升**：原先只能剪课程，今年剪宣传片类也像模像样。
+- **客户反馈**：杨晶项目其他人做不了，她完成后客户说"你还是让那个小姑娘来做"。
 ### 张文倩
-- **综合能力**：编导岗位，需沟通能力与专业水平兼备，表现高出老板期待。
-- **项目完成**：宁波等较难项目老板原以为干不了，但均完成。
-- **提升空间**：因年龄和工作年限，经验与职场感觉有所欠缺。
+- **综合评价**：编导岗位，综合能力强（需沟通能力+专业水平），表现高出老板期待。
+- **项目成果**：宁波等较难项目老板原以为干不了，但人家完成，出乎意料。
 ### 市井
-- **技术标杆**：后期方面技术标杆，2022年后虽其他人也能做，但"依然是在座的最好的没有之一"。
-- **品质**：从更高品质来说依然最好，能攻坚克难。
+- **综合评价**：后期技术标杆，"最好的没有之一"，品质上依然最高。
+- **参与情况**：尊重其个人意见，尽量不麻烦其参与项目，但必要后期会议仍会参加。
 ### 钱德峰
-- **工作强度**：后半年拍摄密集，两个月连轴转没有一天休息；除拍摄外还安排拍摄人员。
-- **额外贡献**：主动建议办停车券、设备更新等运营层面事项，非本职工作但关心公司发展。
-- **提升空间**：期待更强的执行能力、项目或沟通谈判能力。
+- **综合评价**：元老级人物，后半年拍摄非常密集，甚至两个月连轴转没有一天休息。
+- **额外贡献**：除拍摄外还安排拍摄人员；主动建议办停车券、设备更新等运营层面事项，关心公司发展。
+- **提升空间**：期待更强的执行能力（项目、沟通谈判）。
 ### 徐武安
-- **工作表现**：灵光、眼里有活，去警察学院驻场一人孤苦伶仃，客户反馈从初期"经验欠缺"转为认可"挺灵的"。
-- **技术水平**：拍摄和后期技术过关，拍摄技术好于后期。
+- **综合评价**：灵光、眼里有活，拍摄和后期技术水平过关，拍摄技术好于后期。
+- **驻场表现**：去警察学院驻场，一人孤苦伶仃非常辛苦，初期被质疑经验欠缺，后来客户反馈"挺灵的"。
 ### 宋俊逸
-- **编导能力**：入职两三个月（10月），第一个活为宁波两分钟小宣传片，交稿效率高，"行家一出手便知有没有"。
+- **综合评价**：入职两三个月（10月），编导岗位，第一次安排宁波两分钟小宣传片活，很快交稿，老板评价"行家一出手便知有没有"。
 - **项目表现**：后续监狱、财经等项目未出现任何问题，"交给他是完全放心的"。
 ### 张扬
-- **综合评价**：公司邀请来的人才，入职半年，职业态度和工作能力有目共睹，基本达到期待；老板称"2023年干到最有价值的一件事就把他招进来"。
-- **奖项**：获最佳新人奖。
+- **综合评价**：公司邀请来的人才，入职约半年，职业态度和工作能力有目共睹，基本达到期待。
+- **老板评价**：2023年干得最有价值的一件事就是把他招进来。
+- **待遇**：给予比较有诚意的待遇。
+### 林海腾
+- **综合评价**：对运营层面有重要作用，上传下达，员工声音通过其传达给老板。
+- **奖项**：获特别贡献奖，奖金为单项奖中最多；辛苦程度最大（半夜、周六周日被侵占最多），负责执行层面救火、沟通协调。
 ### 李国宇
-- **拍摄水平**：公司内算比较高，能胜任稍高难度工作。
-- **后期能力**：有灵性、能听懂指导，理工项目初剪后被要求修改，最终完美交差。
+- **综合评价**：干满一年，拍摄水平在公司算较高，能胜任稍高难度工作。
+- **后期能力**：后期有灵性、能听懂，剪理工项目第一遍不理想，经沟通后完美交差。
 - **提升空间**：沟通能力需提升。
 ### 张启
-- **商务表现**：表现高于老板预期，性格外向，有主观能动性，主动联系客户打电话。
-- **支持情况**：老板给予支持较少，几乎没什么项目，老板表示后续会考虑给予更多支持。
-### 林海腾
-- **运营作用**：上传下达，传达员工声音给老板；后期安排是繁重工作。
-- **辛苦程度**：加班侵占时间最多、最操心，执行层面救火、沟通协调。
-- **奖项**：获特别贡献奖，奖金为单项奖中最多。
-### 后期部门整体
-- **技术分级模糊化**：往年后期人员间有明确分级，今年分级模糊，效率整体差不多，制作能力提升。
-- **工作强度**：后半年基本都在加班，包括晚上和周末，高强度下仍保证质量，有怨言但继续干，老板评价为"职业操守"。
-- **加班原因**：老板归因为人员不足，判断失误未及时招合适人数。
-### 拍摄部门整体
-- **外援成本**：请外援拍摄成本高，内部人员参与拍摄意愿低，钱德峰建议可尝试内部人员参与拍摄以提升收入。
-- **工作态度**：拍摄小伙子干事情积极，对比外聘助理"干活都得劲"。
-## 制度与流程
-- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元，今年约1000元；干满一年以一个月基本工资为基准，无大纰漏可更高；超过一年主要考虑当年表现，不再过多考虑年限；年限长且满意者有较高预算，实际拿到约2-3万，预算可达大几万。
-- **奖项评选机制**：奖项评选有竞争性，同级别框出2-3人，2选1或3选1；最佳新人奖、最佳进步奖含鼓励成分，后期独挡一面奖、最佳员工奖、特别贡献奖完全出于肯定。
-- **颁奖侧重说明**：年终奖和颁奖对后期部门有所侧重，老板表示这是唯一愿意解释的发放原因。
-- **仪式感改进**：去年李海腾建议公司欠缺仪式感，今年认真对待，定制皮质证书（40元/本含设计费），字体经认真核对。
+- **综合评价**：干了一年的商务，表现高于老板预期，性格外向，有主观能动性，主动联系客户打电话。
+- **支持不足**：老板承认给他的支持较少，几乎没什么项目，后面会考虑给予更多支持和帮助。
+### 后期团队整体
+- **工作强度**：2023年整体劳累程度比去年差，种类比去年多，后半年基本都在加班，很少正常休息。
+- **能力提升**：后期人员之间明确分级模糊化，效率整体差不多，制作能力有进步，整体技术提升。
+- **职业操守**：高强度工作下虽有怨言但仍接着干，保证质量，林海腾评价"非常不容易"。
+### 拍摄团队整体
+- **工作态度**：拍摄人员干事情永远很积极，不会摸鱼，与外聘助理形成对比。
+- **成本建议**：钱德峰提出部分外援拍摄可由公司内部人员完成（如按个机位、保证机器不关机），内外价格差很多，建议尝试内部拍摄以提升收入。
 # 亮点事项
-- **短视频账号突破性增长**：视频号粉丝从3月1日的700人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，增长拐点始于6月20日第一条外出拍摄的对话视频；账号变现课程评分达7.5分（满分10分），视频号直播4-5场，平均在线人数5000+，前100人平均在线50分钟以上。成功原因在于运营郭东辉在潘老师10次劝退的情况下坚持不放弃，并以**破釜沉舟的心情说服潘老师到外面拍摄**，同时外部公司挖角带来的压力促成了这一关键决策。
-- **后期团队整体能力跃升**：后期人员之间原有的明确分级今年模糊化，整体效率趋同、制作能力提升，安排没做过的人硬着头皮接活也能完成，不需要额外操心；后半年基本都在加班且能保证质量，高强度下虽有怨言但仍坚持完成，被评价为职业操守。
-- **新员工超出预期**：红叶子入职两三个月即获政委「很难招到的人才」评价——既懂技术又懂英语且有把事情做好的精神头，连填工资表都会在意见栏写如何改进项目；张扬入职半年基本达到期待，老板称「2023年干到最有价值的一件事就是把他招进来」；宋俊逸第一次安排宁波两分钟宣传片任务即快速交稿，老板评价「行家一出手便知有没有」。
-- **商务部门业绩达标**：实打实项目约300万元，加上入围等应更多；张启表现高于预期——本以为害羞实际外向，有主观能动性，会主动联系客户打电话。
-- **奖项设置增强仪式感**：今年首次认真对待颁奖仪式，设置最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李不续）、最佳员工奖（游腾宇）、特别贡献奖（李海腾）共5项6人，证书为皮质定制（40元一本含设计费），评选经认真讨论、2选1或3选1竞争产生；老板称这是回应员工「欠缺仪式感」的建议，奖金相对可观。
-- **员工给予老板信心**：外部搞运营的人惊讶公司能做这么久，老板表示「因为有这样的员工，我要把这个事搞成了才能对得起人家」，员工的表现反过来给了老板信心，项目从数据或前景上向好。
+## 账号运营突破与平台增长
+- **账号从低谷到起色**：视频号粉丝从3月1日的719人增长至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，转折点始于6月20日第一条外出拍摄的对话视频。
+- **关键动作——破釜沉舟说服外出拍摄**：6月20日前潘老师已10次提醒运营「出去找工作吧」，运营在收到外部公司邀约后，以破釜沉舟的心情说服潘老师尝试外出拍摄，加上forty加入，项目得以坚持并迎来转折。
+- **坚持不放弃的韧性**：运营认为「如果要放弃应该是黄大师那边去说」，因此一直坚持；老板转述同行评价「你们居然能做这么久，如果是他们这种状况可能就放弃了」。
+- **数据驱动的直播策略**：视频号直播4-5场，平均在线人数5000+，前100人平均在线时长50分钟以上；运营每晚8-9点抽1小时刷竞品直播间（侃哥、巧克力、克瑞斯金等英语老师），研究内容与互动方式。
+- **账号变现能力初步建立**：课程变现按十分制自评达7.5分（含0.5分期待空间），直播已具备变现条件但尚无课程支撑。
+## 员工表现超出预期
+- **刘腾宇获最高评价**：老板评价其为「评价最高的，没有之一」，职业性、专业性、纪律性俱佳，迟到几乎没有，请假严格按规定并提前安排工作；客户罗峰反馈「如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了」；重要活安排给刘腾宇后老板「把这个活忘了，肯定不会有任何问题」；因林海腾4分钟夸赞，年终奖在既定标准上再拉一档，刚满一年却给老板「干了5、6年老员工」的错觉，年终奖「可能还会翻倍」。
+- **红叶子获政委高度评价**：政委「相对严苛」却给予「非常高的评价」，称「很难招到这样的一个人才，既懂技术又懂英语，而且有把事情做好的精神头」，在工资表意见栏认真写项目改进建议。
+- **张扬是2023年最有价值的事**：老板称「2023年干到最有价值的一件事就把他招进来」，其职业态度与工作能力「基本上达到了我们的期待」，并带来三维制作能力——往年二维三维均外包，现在可内部解决。
+- **宋俊逸首次安排活即获认可**：老板安排宁波两分钟宣传片，宋俊逸很快交回文稿，老板评价「行家一出手便知有没有」，后续监狱、财经等项目「交给他是完全放心的」。
+- **张文倩完成老板以为会黄的活**：宁波等难度较高的项目老板「以为就黄了」，但张文倩完成且「出乎我的意料」。
+- **后期整体能力提升**：林海腾反馈今年后期人员分级模糊化，效率整体接近，制作能力提升，高强度加班下仍保证质量，「有怨言但还会接着干」体现职业操守。
+## 仪式感建设与员工激励
+- **认真对待颁奖仪式**：老板承认往年欠缺仪式感，今年认真准备——证书为皮质、40元一本含设计费，字体经认真校对；设最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李不续）、最佳员工奖（游腾宇）、特别贡献奖（李海涛，奖金最多），共6人5项奖。
+- **评奖标准明确且有竞争性**：每项奖2选1或3选1，「如果你没拿到，并不代表你就是能力不行，但至少证明你不突出」；最佳员工奖将所有人名列在一起认真讨论，非偏向单一部门。
+- **员工激励与补偿**：年终奖总额226,000元，最高2-3人到手超20万；对短视频部门受委屈给予补偿；加班在年终奖中补贴一两千元；老板自写100元红包奖，抽奖设15个奖品（充电宝、观影券、洗头膏等），另提供当天看电影/吃饭额度内报销福利。
 # 不足事项
 ## 成本控制与利润率
-- **成本控制非常差**：老板明确指出成本控制是公司最大的问题，2023年实打实花出去的钱（含人员工资、外援配音、字幕、租机器）达390万元，利润率仅24%或27%，老板评价为「非常不可观」。
-- **根因在老板管理**：老板自认**根源问题是老板对业务关心或关注不够、不够雷厉风行，出现问题没有及时解决**，并称这是「最大的癌症的问题」。
-- **结余缩水**：公司总量在提升、员工拿到钱在提升，但成本也在往上跑，公司结余到账是往下跑的；另有百来万款项未收回，结余「稍微缩水」。
-## 短视频账号运营
-- **账号尚未变现**：短视频账号虽粉丝大幅增长（视频号从700人增至8万、小红书从2000+增至6.4万、抖音从2000+增至5.7万、B站从3.1万增至7.6万），但账号变现重点项目**没有完成**；变现课程评分自评7.5分（满分10分），其中0.5分为期待空间。
-- **前期项目濒临放弃**：运营郭东辉自述6月20日之前，潘老师已多次（记不清具体次数，约10次）提醒「你出去找工作吧，我这个项目我不想干了」；郭东辉认为不应由自己放弃，坚持到说服潘老师外出拍摄后项目才有起色。
-- **一人多岗精力受限**：郭东辉指出正常情况下一个公司是一个人拿一个账号、一个平台不同平台一人负责，但实际是**他一人负责各平台运营**，需处理课程上架、开店、开企业店等无经验事务，有时精力不充沛。
-## 后期部门加班与人员配置
-- **加班严重**：后期负责人林海腾（音）指出今年尤其是后半年基本都在加班，很少正常休息，包括晚上和周末；高强度工作下大家有怨言但仍继续干。
-- **根因是人员不足**：老板承认**加班是老板的锅，本质是没有及时招更合适或更合适人数的人员**；商务给活是连续信号，但业务有断续，造成「不需要招这么多人」的错觉，同时平时积累的人脉资源又不确定，导致判断失误。
-- **外援成本高**：员工钱德峰指出有一段时间请了很多天外援，但有些事公司内部人员就能搞定（如上午谁有空去按个机位、让机器不关机），结果公司凑不出这样的人；外援拍摄与内部人员拍摄两边价格差很多。
-## 拍摄参与意愿
-- **内部人员参与拍摄意愿低**：钱德峰反映喊人参与拍摄时，很多人以「没空、很忙、不想去」为借口推脱；老板回应称被领导问到时应至少解释手头忙什么或勉为其难安排一下，直接说「没空」非常不职业。
-- **拍摄与后期奖金侧重差异**：老板承认年终奖和奖项发放上**后期比前期（拍摄）少一截**，这是老板唯一愿意解释的发放原因；老板同时表示即使如此，拍摄人员所得也不会比后期少，已掌握平衡。
-## 商务部门支持
-- **老板支持不足**：老板评价商务张启时承认，作为老板给商务的支持比较少，张启几乎没什么项目，老板只是帮着聊一聊或打理；后续会考虑给予更多支持和帮助。
-## 员工个人自评未达预期
-- **张启自评未达预期**：张启自述2023年对自己预期而言**没达到自己的预期**，原因包括效率、时间，以及项目上对同事和甲方的沟通做得不太好。
+- **成本支出过高**：2023年实打实花出去的钱（人员工资、外援配音、字幕、租机器等）达390万元，利润率仅约24%或27%，老板明确表示**成本控制非常差**，是公司最大的问题。
+- **结余缩水**：公司总量在提升、员工拿到钱在提升，但成本也在往上跑，公司结余到账往下跑；另有百来万没收回来，结余稍微缩水。
+- **根因——老板管理问题**：老板自认这是"最大的癌症的问题"，根源在于**老板对员工关心或关注不够，不够雷厉风行，出现问题没有及时解决**。
+- **成本控制议题延后**：成本控制问题明年开会时再讨论，本次未给出具体改进方案。
+## 加班与人员配置
+- **加班现象严重**：后期部门今年尤其是后半年基本都在加班，很少正常休息，晚上、周末均被占用；林海腾提到今年整体劳累程度比去年差、种类比去年多。
+- **根因——人员不足**：老板承认加班"是老板的锅"，本质上是**没有及时招更合适或更合适人数的人员**；商务给活是第1信号，业务断断续续造成"不需要招这么多人"的错觉，但平时积累的人脉资源又不确定，导致判断失误。
+- **加班补贴**：年终奖商议时对加班有所考虑，在既定标准上再补贴一部分，可能有**一两千元**的考虑。
+## 账号运营与变现
+- **账号尚未变现**：短视频账号虽在多个平台有显著涨粉（视频号从719人增至8万、小红书从2000+增至6.4万、抖音从2000+增至5.7万、B站从3.1万增至7.6万），但**账号变现重点项目没有完成**，课程变现程度自评约7.5分（满分10分），其中0.5分为期待空间。
+- **直播有量无课**：视频号直播4-5场，平均每场在线人数5000人以上，前100人平均在线时长50分钟以上，但**目前没有课程，尚不能进行变现**。
+- **前期困境**：6月20日之前，潘老师多次（约10次）提醒郭东辉"出去找工作吧，这个项目我不想干了"；郭东辉因有其他公司挖角，以破釜沉舟的心情说服潘老师到外面拍摄，加上forty加入，项目才坚持下来。
+- **根因——公司限制**：老板承认"合作的对象和公司限制了这个部门的发展"，公司对郭东辉的发挥有所限制，应表示歉意。
+## 拍摄外援成本
+- **外援成本偏高**：钱德峰指出有一段时间请了很多天外援，但部分工作公司内部人员即可完成（如上午谁有空去按个机位、让机器不关机即可），内部却凑不出人；外援拍摄与内部人员拍摄两边价格差很多。
+- **内部参与意愿不足**：钱德峰反映喊人参与拍摄时，很多人以"没空、很忙、不想去"为由推脱；老板回应称被领导问到时应解释手头工作或勉为其难安排，直接说"没空"非常不职业。
+## 员工个人未达预期项
+- **郭东辉（运营）**：一人负责多个平台运营（正常情况下一个公司是一个平台一个人负责），精力不充沛，需自行学习课程上架、开店、开企业店等无经验事务；6月前处于"混日子"状态，没有收获感、成就感、幸福感。
+- **欧阳（后期）**：刚满一年，有学习能力和进步，但**沟通能力需再爬坡**。
+- **徐艺玲（后期）**：技术有进步（从只能剪课程到能剪宣传片类），但老板感觉其"不开心"，更高期待明年再说。
+- **张文倩（编导）**：表现超出老板期待，但因年龄和工作年限问题，经验或职场感觉有所欠缺。
+- **市井（后期）**：技术标杆地位不变，但老板期待其能参与解决部分较难的问题，此前有聊过项目但尊重其个人意见。
+- **钱德峰（拍摄）**：拍摄密集、两个月连轴转无休息，个人时间被侵占较大；老板期待其有**更强的执行能力**（项目、沟通谈判方面）。
+- **李国宇（拍摄）**：拍摄水平较高，但部分外援成本源于技术水平达不到，期待其能达到更高段位；后期有灵性但需"逼一顿"才能完美交差；**沟通能力有问题且很严重**。
+- **张启（商务）**：表现高于预期、有主观能动性，但老板给的支持比较少，几乎没什么项目，老板后面会考虑给予更多支持和帮助。
+- **张扬（商务）**：基本达到期待，但老板表示"有些问题不是个人的问题，是老板的问题"，具体问题明年再说。
+- **林海腾（后期/运营协调）**：安排活时有问题——有些活不知道安排谁或谁能完成，只能硬着头皮安排没做过的人；老板承认加班问题与人员配置判断失误相关。
+## 部门层面不足
+- **短视频部门**：账号尚未变现，变现是明年期待；老板将投入更大精力并给予足够重视。
+- **执行部门**：项目没做砸过、满意度尚可，但老板期待明年能更多进行组织协调，提高效率、减少休息时间侵占。
+- **商务部门**：结果基本达到预期，实打实项目约300万元左右；老板承认今年对部门**支持、管理、关心不够**，明年会反思。
+- **老板自我批评**：对员工关心或关注不够、不够雷厉风行、出现问题未及时解决；对部门支持、管理、关心不够；未及时招合适人数的人员导致加班严重。
 # 改进计划
-## 成本控制与经营改善
+## 成本控制与经营健康度
 - **针对成本控制差、利润率仅24%或27%的问题**：老板表示明年开会时再讨论成本控制的具体方案，未给出具体措施。
-- **针对老板管理不足、对员工关心不够、不够雷厉风行、出现问题未及时解决的根因**：老板在部门展望中承认今年对商务部门给予的支持、管理或关心不够，表示明年会反思这个问题。
-- **针对公司有百来万未收回款项、结余缩水的问题**：老板未提出具体催收或回款计划。
-## 短视频账号发展与变现
-- **针对短视频账号尚未变现、重点项目未完成的问题**：老板表示明年期待账号能开始变现，作为老板会投入更大精力做这个事情，并给予足够重视。
-- **针对短视频账号运营中说服老板难、说服自己更难、精力分散等困难**：运营郭东辉提出坚持与破壳经验，老板对部门整体表示认可，未给出具体改进动作。
-## 后期部门加班与人员配置
-- **针对后期部门加班严重、人员不足是最大因素的问题**：老板承认本质上是没有及时招更合适或更合适人数的人员，属于判断失误，但未给出明年具体的招聘计划或人数目标。
-- **针对加班补贴问题**：老板表示在年终奖商议时已考虑加班因素，在既定标准上再补贴一部分，可能有一两千元的考虑，已体现在年终奖发放中。
-## 拍摄外援成本与内部参与
-- **针对拍摄外援成本高、内部人员参与拍摄意愿低的问题**：员工钱德峰建议尝试让内部人员参与拍摄，一方面提升收入，另一方面体验拍摄工作；老板回应称去年已说过拍摄性价比相对高，没有阻止任何人参与，但确实存在安排不开的原因，期待大家都能参与拍摄，明年会往这个方向靠，希望每个人都能参与一下。
-- **针对被问到拍摄任务时直接说“没空”的不职业现象**：老板指出如果领导问到，应起码解释手头上忙的东西，或勉为其难安排一下，直接说没空是非常不职业的。
-## 商务部门支持
-- **针对商务部门项目获取中老板支持较少的问题**：老板表示张启（商务）几乎没有什么项目，老板帮他聊了聊或帮着打理，后面会考虑给他更多的支持和帮助。
-## 组织协调与员工关怀
-- **针对执行部门辛苦程度高、休息时间被侵占的问题**：老板表示期待明年老板能够更多地进行组织协调，提高效率，提升大家工作的开心程度，尽可能少地侵占大家的休息时间。
-- **针对公司欠缺仪式感的问题**：今年已认真对待，制作皮质证书（40元一本含设计费）、设置奖项并发放红包，明年未提及进一步改进。</t>
+- **针对公司有百来万款项未收回、结余缩水的问题**：老板在会议中提及该现象，但未给出明确的催收或改善计划。
+## 管理方式与支持力度
+- **针对老板对员工关心关注不够、管理不够雷厉风行、问题未及时解决的问题**：老板承认这是成本问题的根源，并表示明年会反思对部门支持、管理、关心不够的问题。
+- **针对执行部门休息时间被侵占、加班多的问题**：老板期待明年能更多进行组织协调，提高效率，尽可能减少侵占大家休息时间。
+- **针对加班问题中人员不足这一最大因素**：老板承认未及时招聘合适人数是判断失误，但未给出明年具体的招聘计划或人数目标。
+## 业务发展与部门能力
+- **针对短视频账号尚未变现的问题**：老板期待明年账号能开始变现，并表示会投入更大精力、给予足够重视。
+- **针对外援成本高的问题**：发言者7建议尝试让公司内部人员参与拍摄，以降低外援支出并提升收入；老板回应称期待大家都能参与拍摄，明年会往这个方向靠，希望每个人都能参与。
+- **针对部分拍摄任务技术水平达不到、需依赖外援的问题**：老板对李国宇提出期待，希望其能达到更高技术段位，能胜任高难度拍摄，并向段位高的人多多学习。
+- **针对后期人员分工模糊、安排活时不确定谁可完成的问题**：发言者11反映今年安排活有困难，但未给出具体改进方案。
+- **针对商务部门项目支持不足的问题**：老板表示后面会考虑给张启更多的支持和帮助。
+## 员工个人发展
+- **针对欧阳沟通能力需提升的问题**：老板提出期待其沟通能力再爬坡，并希望其保持进步与热爱。
+- **针对李国宇沟通能力问题**：老板提出更高期待，希望其提升沟通能力。
+- **针对市井参与项目的问题**：老板表示尊重其个人意见，但期待其能解决一部分公司认为比较难的问题。
+- **针对钱德峰执行能力问题**：老板提出期待其有更强的执行能力，包括项目执行和沟通谈判。
+- **针对徐武安后期技术水平弱于拍摄技术的问题**：老板指出该现象，但未给出具体提升计划。
+- **针对宋俊逸编导岗位**：老板表示该岗位明年可能发挥更大价值，未给出具体计划。
+- **针对张扬**：老板表示如果出现问题，是老板或制度管理沟通的问题，具体问题明年再说。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/7168</t>
+          <t>24562/8276</t>
         </is>
       </c>
     </row>
@@ -2099,78 +2104,82 @@
       <c r="C5" t="inlineStr">
         <is>
           <t># 全文摘要
-本次专项讨论会由办事处组织，小区业委会代表与物业方就服务质量、欠费、业主大会召开及法律诉讼等问题进行协调。业主代表提出，小区业主自发接龙已有200来位业主，主要诉求是召开业主大会表决物业去留；物业方则称事先未接到沟通，且已决定本月起诉业委会，认为诉讼期间无法召开业主大会。双方就程序合法性激烈争论，未达成一致。业主代表列举小区10条问题，涵盖门柱灯、水系、监控、绿化、围墙、民生配套、雨水倒灌及人员配备等；物业方逐条回应，称部分问题属地产责任、费用不足或超出服务范围，双方对责任归属分歧严重。物业方强调业主欠费导致无力整改，业主方认为服务不达标是欠费原因，陷入循环争论。物业方宣布已与集团法务沟通，本月将起诉业委会，并称已掌握业主群内证据；业主代表表示若物业起诉将反诉。会议最终未达成一致，业主方表示将正常推进业主大会，物业方坚持走法律程序。关键数字：业主自发接龙200来位业主、物业称业主欠费170多万、园区年收入100来万、人工成本100多万、物业办公室人员从近10人减至4人。
+本次会议为小区业主与物业的专项协调会，由办事处领导（发言者3）主持，物业方（发言者2、发言者7）与业委会及业主代表（发言者4、发言者5等）参与，旨在协调业主提出的10条服务问题及业主大会召开事宜。会议围绕业主大会召开与表决、小区服务问题清单、物业费与资金问题、法律诉讼与反诉四个板块展开。业主代表列举入户门柱灯未开启、监控几乎全部损坏、雨水倒灌自2019年未解决、物业人员从办公室近10人减至4人等10条问题，要求召开业主大会表决物业去留；物业方逐条回应，强调业主欠物业费170多万、年收入100多万而人工成本100多万、每年亏损，无力承担维修，并宣布本月将起诉业委会。业主方表示将正常推进业主大会，若物业起诉将反诉。双方未达成一致，会议无实质结果。
 # 分段速览
-## 00:10-05:04 开场与背景铺垫
-会议开场后，发言者2首先谈及小区供暖开户费问题，指出园区从建设到后期从未验收，开户费应由地产出资并将管道交接给供暖公司，但至今未完工未验收，导致多数人误认为是物业责任。发言者2强调开发商已缴纳配套费，但资金流向不明。发言者3确认费用已交清。发言者2随后提到维修事项需扩大范围，并提及业主不愿退房、对小区抱有希望，二期补助比例约29%，以及业主自发组织、热心业主参与等情况。
-## 05:36-10:14 业主诉求与组织情况
-发言者4介绍业主自发组织了接龙活动，约200来位业主参与，主要议题是召开业主大会，认为业委会或业主个人无权决定撤换物业，应由全体业主表决。发言者2询问工作群数量，发言者4回应业委会工作组仅1个群，准业主分5个群，共6个群，由筹备组6人分别联系。发言者4补充接龙群是交房时老邱哥建立的业主群，已有5、6年历史。发言者2强调讨论需有明确目的和程序，不能失控。
-## 10:14-18:01 会议目的与程序之争
-发言者2强调成立业委会和召开业主大会应以讨论为主、表决为辅，最终结论以表决为主。发言者5总结接龙业主心声：一是要求解决小区存在问题，二是若整改达不到效果，可考虑招标更换物业，原物业也可参与投标。发言者5提及业主提出11个问题。发言者2指出按正常流程，召开业主大会前应与物业公司沟通，但物业事先未接到任何通知，并质疑接龙是有组织的，物业未参与议题制定。
-## 18:01-22:08 物业宣布起诉
-发言者2郑重声明，鉴于双方存在违法情况，已与集团法务沟通，本月将正式起诉业委会，并称起诉期间业主没有行使表决权的义务和责任。发言者2表示已掌握业主群内证据，欠费周期超过一年的业主不能成为业主代表，上午9:52已与高级人民法院通话，也与滨城区人民法院沟通，有沟通记录。发言者2指出业委会从选举到后期决策存在违法行为，包括在业主群煽动、撬门等，将起诉业委会及保洁业主代表。
-## 22:08-31:22 业主列举十项问题
-发言者4逐条列举小区问题：①入户门柱灯从未开启；②内部水系从未运行；③售楼处迎宾水系从未开启；④监控几乎全部损坏，上月进贼时110和刑警大队未能获取数据；⑤监控室从王艳芳上任后无人值班，一键直达功能荒废；⑥绿化维护差，去年多棵树死亡，物业管家称要等明年看能否发芽；⑦北边围墙用烂铁皮遮挡且有缺口，社会人员可随意进出，物业承诺定制围挡但未兑现；⑧快递柜、直饮水、宽带、暖气开户等民生配套多年无进展；⑨雨水倒灌自2019年多次造成财产损失；⑩物业人员从办公室近10人减至4人，维修从5人减至2人。
-## 31:22-38:01 物业逐条回应
-发言者2逐条回应：①门柱灯因能耗成本高未开启，业委会曾承诺协助收费后修复；②水系从交付起存在质量问题，属地产维修责任；③监控损坏因费用超运营承担，园区年收入100来万、人工成本100多万，每年亏损；④进贼时物业已将监控画面截取给派出所和刑警；⑤绿化问题因业委会10月才成立，冬季无法更换；⑥北边围墙在红线外属违建，物业无处理义务，曾协调定制但因费用高未成；⑦民生配套属地产前期配套；⑧雨水倒灌是地产设计问题；⑨人员配备不足因地产补亏款未结。发言者2称业主欠费170多万，回款40万可解决部分问题。
-## 38:01-48:00 矛盾激化与对峙
-发言者4反驳物业服务不应有滞后性，问题从交房起就存在，非物业入驻后才出现。发言者2坚持走法律程序，称起诉期间无法更换物业公司。发言者4称业委会成立之日自动解除物业合同关系，双方就程序合法性激烈争论。发言者3指出无钱无法整改、业主不愿缴费形成恶性循环。发言者4提出可能集体起诉物业要求返还部分物业费。发言者8质疑物业窥探业主隐私，表示将反诉。
-## 48:00-01:03:16 调解失败与收场
-发言者7确认已与集团法务沟通，今日操作起诉手续，已截屏保存业主群动态。发言者4举例物业经理在进贼时回应「你交物业费了吗」，并称「不交物业费就上你家吃饭」，发言者7否认并要求拿出录音。发言者3建议物业拿出真实行动赢得业主信任，发言者7称业主欠费170多万、公司持续亏损，地产公司已申请破产。双方未能达成一致，发言者4表示将正常推进业主大会，发言者2称会议未解决实质性问题，会议结束。
+## 00:10–05:37 开场与费用背景
+会议开场后，发言者2首先谈及小区供暖开户费问题，指出园区从建设至今未验收，开户费应由地产出资并将管道交接给供暖公司，但至今未完工，导致责任归属不清。发言者2称开发商已缴纳配套费等全部费用，但具体去向不明，发言者3确认费用已交清。发言者2还提到业主对退房态度不一，发言者4补充业主因买房满怀希望而不愿退房。此段以费用与开户问题为讨论起点，未形成结论。
+## 05:37–10:14 业主自发组织与缴费情况
+发言者2介绍业主自发组织情况，称有热心业主牵头，涉及约13万元费用，业主自发交费400元。发言者4说明二期三期实际交费业主约20来户。发言者2提到部分业主担心管道问题影响明年供暖，希望今年解决。发言者5表示业主有诉求但表达方式有限。此段围绕业主自发组织、缴费规模与对供暖的担忧展开，发言者2强调需坦诚沟通、避免对立。
+## 10:14–16:59 业主大会程序讨论
+发言者2强调成立业主委员会应坦诚相待、不暴露敌对情绪，并询问工作群数量。发言者4说明业委会工作组仅1个群，准业主分5个群，共6个群，由筹备组6人各联系一部分业主；接龙群为老邱哥所建，交房时即有，已存在5、6年。发言者4建议尽快召开业主大会由全体业主表决，发言者2质疑接龙200人的代表性，强调需按程序讨论。发言者5总结接龙业主心声：要求整改小区问题，若整改不了可招标，原物业也可参与投标。
+## 16:59–22:08 物业方宣布起诉
+发言者2代表物业方正式声明：召开业主大会前应与物业公司沟通，但物业未接到任何通知；鉴于双方成立及工作过程中存在违法情况，已与集团法务沟通，本月将正式起诉业委会，并称欠费人员不能成为业主代表。发言者2称已掌握业主群内证据，上午9:52与高级人民法院通话，也与滨城区人民法院沟通，起诉对象包括业委会及保洁业主代表。发言者5强调业主大会开与不开是必须之事，关键在于能否改善现状。
+## 22:08–31:22 业主列举10条问题
+发言者4逐条列举小区问题：①入户门柱灯从未开启；②内部水系从未开启；③售楼处迎宾水系从未开启；④监控几乎全部损坏，上月进贼后110与刑警均未从监控获得数据；⑤监控室24小时值班及一键直达服务自王艳芳上任后荒废；⑥绿化维护不力，去年死树多棵，物业管家称等明年看能否发芽；⑦北边围墙用烂铁皮遮挡且有缺口，社会人员可随意进出，物业承诺定制围挡后未兑现；⑧快递柜、直饮水机、宽带、暖气开通等民生问题无进展，由业委会全程办理；⑨雨水倒灌自2019年存在，业主多次反映无果；⑩物业人员从办公室近10人减至4人，维修从5人减至2人。
+## 31:22–38:53 物业方逐条回应
+发言者2逐条回应：①门柱灯未亮因能耗成本过高，物业无法运营，曾与业委会沟通，业委会承诺支持缴费后修复；②水系从交付起存在质量问题，泵无法运转，属地产配套未完成，由地产维修；③④监控损坏因无费用，物业年收入100多万，人工成本100多万，每年亏损，随时可查账；⑤民警进园区时物业已将监控画面截取给派出所和刑警；⑥绿化死亡因业委会10月成立后已入冬季，换树责任不明；⑦北边围墙属红线以外且涉及违建官司，物业无权处理，曾协调定制但费用太高未成；⑧民生配套属地产前期配套，开通费用由业主承担；⑨雨水倒灌因园区地势四周高中间低，超出排水承载，属地产设计问题；⑩人员配备因地产补亏款未结，20来人年成本100多万，维修费今年花了几十万。
+## 38:53–46:14 双方对峙激化
+发言者4反驳物业服务无滞后性，不应先收钱再服务，并指出门柱灯、水系、监控等问题从交房起就存在，非物业近期资金困难所致。发言者2强调今天目的是协调业委会成立问题，并非要求换物业。发言者4表示无讨论必要，基本决议是换掉物业，发言者2称同意换物业但前提是结清费用，并称案件存续期间无法换物业。发言者4称业委会成立之日即自动解除物业合同关系。发言者2表示物业已掌握证据，将依法维权。
+## 46:14–01:03:16 调解失败与收场
+发言者3（办事处领导）指出问题根源是没钱，服务不整改业主不缴费，形成恶性循环，建议双方冷静沟通。发言者4提出可能集体起诉要求返还部分物业费。发言者8质疑物业窥探业主隐私，称若物业起诉将反诉。发言者4指责物业经理曾对业主说「不交物业费就上你家吃饭」，发言者7否认并要求拿出录音。发言者3建议物业拿出实际行动赢得业主信任，发言者7称业主欠物业费170多万，要求先回款40万再维修。双方就地产破产、物业费与服务先后问题争执不下，发言者2宣布会议到此为止，未解决实质问题。
 # 要点梳理
-## 业主大会召开与物业去留
-- **业主接龙**：小区业主自发组织接龙，约200来位业主参与，主要议题是召开业主大会。
-- **群组构成**：业委会工作组群1个，准业主群5个，共6个群；接龙群为交房时业主自发建立的业主群，已存在5、6年。
-- **业委会立场**：业委会成员表示，业委会或业主个人无权决定撤换物业，需通过业主大会由全体业主表决。
-- **物业方程序质疑**：物业方称事先未接到任何关于召开业主大会的沟通，认为接龙有组织、议题不明，且未参与。
-- **物业方起诉声明**：物业方称已与集团法务沟通，本月将正式起诉业委会，并称已掌握业主群内证据、已截屏保存。
-- **欠费人员资格**：物业方称欠费人员不能成为业主代表，顶名者也不能，将依法追究责任。
-- **合同关系争议**：业主代表称业委会成立之日即自动解除与物业的合同关系；物业方称起诉期间无法更换物业公司。
-- **会议基调**：办事处代表建议双方坦诚沟通、不暴露敌对情绪，物业方称「不希望把矛盾往深一步拉」。
-## 小区问题清单与物业回应
-- **门柱灯未开启**：业主称入户庭院门柱灯从未开启；物业称因园区能耗成本过高、物业公司无法运营，业委会曾承诺协助收费后修复。
-- **水系未运行**：业主称内部水系及售楼处迎宾水系从未开启；物业称水系从交付起存在严重质量问题、泵无法运转，属地产配套未完成，维修责任在地产。
-- **监控损坏**：业主称监控几乎全部损坏，上月小区进贼时110派出所及刑警大队未能从监控获取数据；物业称监控损坏因费用超运营承担，园区年收入100来万、人工成本100多万，每年亏损，可公开查账。
-- **监控室服务荒废**：业主称监控室原应24小时值班、门铃有一键直达功能，自王艳芳上任后服务荒废、无人值班；物业称警察进入园区时已第一时间将拍摄画面截取给派出所和刑警，并出示刑警调取监控的照片和记录。
-- **绿化维护差**：业主称去年多棵树死亡，小区门口两侧已知死3棵，曾致电物业管家反映树生病，管家称「经理说了，明年看看能不能发芽」；物业称业委会今年10月成立备案，此后已入冬季，换树责任归属存疑。
-- **北边围墙缺失**：业主称北边用烂铁皮遮挡、最西边有缺口可随意进出，业委会责令整改后物业拆除铁皮再无动作，并称「已定制围挡」但未安装，业主证实并无定制；物业称北边围墙在红线以外、属违建，不在物业服务范围内，曾协调施工单位定做但因费用过高未成，费用本应由物业承担，已与业委会沟通不下5次。
-- **民生配套未解决**：业主称快递柜、直饮水机、宽带覆盖、暖气开户等多年无进展，最终由业委会全程办理；物业称根据建设条例和前期配套要求，属地产前期配套问题，后期开通费用由业主承担。
-- **雨水倒灌**：业主称自2019年起多次造成财产损失，多次反映无进展，明年再有大雨可能再淹；物业称园区地势四周高中间矮、车库设计为斜坡向下，属地产前期设计建设问题，超出物业解决能力。
-- **人员配备不足**：业主称物业办公室从近10人减至4人（含经理），维修人员从5人减至2人；物业称因地产补亏款未结，现项目20来人、一年人工成本100多万，光维修费今年花了几十万。
-## 物业费欠费与资金困境
-- **欠费规模**：物业称业主欠物业费170多万，回款40万可解决部分问题，账上一分钱没有。
-- **经营亏损**：物业称园区年收入100来万，人工成本100多万，不含垃圾清运费、能耗、维修、税费及办公成本，每年亏损。
-- **欠费与服务循环**：业主称服务不达标是欠费原因；物业称欠费导致无力整改，双方陷入循环争论。
-- **集体起诉意向**：业主代表称在最终解决前，可能就交房以来未达成的服务集体起诉物业、要求返还部分费用。
-- **地产破产**：物业称地产公司已申请破产，无法追讨配套费用；办事处代表质疑「申请破产就没有办法了吗」，物业称业委会集体提出是最好办法。
+## 业主大会召开与表决
+- **业主诉求**：小区业主自发组织接龙约200人，主要议题为召开业主大会，表决物业去留。
+- **群组情况**：业委会工作组群1个，准业主群5个，共6个群；接龙群为交房时即建的业主群，已存在5、6年。
+- **业主方立场**：业委会或业主个人无权决定撤换物业，须由业主大会表决；建议尽快召开业主大会让全体业主表决。
+- **物业方质疑**：召开业主大会前应事先与物业公司沟通，但物业方未接到任何通知，也未参与接龙组织。
+- **物业方声明**：欠费人员不能成为业主代表，顶名也不能成为业主代表，相关情况将依法追究责任。
+- **表决方式**：会议讨论以表决为主，而非仅讨论；业主方表示将正常推进业主大会。
+## 小区服务问题清单
+- **门柱灯**：入户庭院门柱灯自交房以来从未开启过，业主认为属应得利益与服务。
+- **水系问题**：内部水系自卖房后从未开启；售楼处门口迎宾水系也从未开启，业主认为水系是小区门脸。
+- **监控损坏**：监控几乎全部损坏，上个月小区进贼，110派出所及刑警大队均未从监控获得任何数据。
+- **监控室服务**：交房时配备24小时值班监控室，门铃有一键直达功能；王艳芳上任后此项服务荒废，监控室无人值班。
+- **绿化维护**：去年死树多棵，小区进门两侧已知死3棵；业主曾报修生病树木，物业管家回复「经理说了，明年看看能不能发芽长绿叶」。
+- **北边围墙**：北边用烂铁皮遮挡，最西边有缺口，社会人员可随意进出；业委会责令整改后物业拆除铁皮但未装新围挡，业主证实物业并未定制围挡。
+- **民生配套**：快递柜、直饮水机、宽带覆盖、暖气开通开户等民生问题多年无进展，最终由业委会全程办理。
+- **雨水倒灌**：自2019年起每逢大雨业主有不同程度财产损失，多次向物业反映要求完整解决办法，至今无进展。
+- **人员配备**：物业办公室最初近10人，现加上经理共4人；维修人员从5人减至2人，人员配备严重不足。
+## 物业方逐条回应
+- **门柱灯**：因园区能耗成本过高，物业公司已无法运营；业委会曾承诺支持全员缴费并协助收费，收上费用后拿出一部分做修复。
+- **水系**：水系自交付起存在严重质量问题，所有泵无法正常运转，属地产配套未完成，由地产维修，不属于物业责任。
+- **监控**：物业公司已与业委会沟通，第一个修的就是监控，但因费用超出运营承担无法实施。
+- **经营状况**：园区保护收入一年100来万，光人工成本就占100多万，不含垃圾清运费、能耗、维修、税费及办公成本，每年亏损，可公开查账。
+- **监控数据**：警察进入园区时物业第一时间将拍摄画面截取给派出所和刑警，有刑警调取监控的照片和记录。
+- **绿化**：业委会今年10月成立并备案，之后进入冬季，换树责任归属存在争议。
+- **北边围墙**：北边围墙在物业服务范围红线以外，且涉及法律官司、本身属违建，物业有权不处理；曾协调施工单位定做但因费用太高未成，费用需物业承担，已与业委会沟通不下5次。
+- **民生配套**：宽带、快递柜、燃气等属地产前期配套问题，按建设条例和前期配套要求，后期开通费用由业主承担。
+- **雨水倒灌**：园区地势四周高中间矮，车库设计为向内斜坡，排水量超出承载范围，需查地产前期设计是否符合规范。
+- **人员配备**：前期人员充足是因地产给了一批补亏款，该款至今未结账；现项目20来人，一年成本100多万，今年维修费花了几十万。
+## 物业费与资金问题
+- **欠费金额**：物业方称业主欠物业费170多万，曾向业委会提出回款40万即可解决部分问题，但账上一分钱没有。
+- **恶性循环**：业主认为服务不达标故不愿交费，物业无钱改善服务，双方陷入僵局。
+- **业主反诉意向**：业主方提出在最终解决前，可能集体起诉要求返还此前未达服务标准的物业费。
+- **物业方指责**：业委会成员在业主群告诉大家不要缴费，与当面承诺协助收费矛盾，物业方称有记录并已联系法院。
 ## 法律诉讼与反诉
-- **起诉决定**：物业方宣布本月正式起诉业委会，包括保洁业主代表，理由为阻碍正常经营、造成物业经济损失。
-- **沟通记录**：物业称上午9:52与高级人民法院通话，有沟通记录；已与滨城区人民法院沟通，均致电。
-- **证据收集**：物业称已在业主群掌握很多证据和依据，业主动态已截屏保存。
-- **反诉表态**：业主代表称只要物业起诉就反诉、拿出证据来。
-- **隐私争议**：业主代表质疑物业截屏业主群动态属窥探隐私；物业称不影响业主正常生活。
+- **物业方决定**：已与集团法务沟通，本月将正式起诉业委会，包括保洁业主代表；已与滨城区人民法院和高级人民法院致电沟通，上午9:52与高级人民法院通话。
+- **起诉理由**：业委会从选举存在违法行为、后期决策及在业主群煽动，不符合业委会行使权利职责，还有撬门行为；以阻碍正常经营、造成物业公司经济损失为由起诉。
+- **证据**：物业方称已在业主群掌握很多证据和依据，业主群动态已截屏保存。
+- **业主方回应**：若物业起诉将反诉并拿出证据；有业主质疑物业窥探业主隐私。
+- **欠费与代表资格**：物业方称欠费周期超过一年的业主不能成为业主代表，顶名也不能。
 ## 结论与决定
-- **物业方决定**：本月正式起诉业委会，理由为阻碍正常经营、造成物业经济损失，已与集团法务沟通。
-- **业主方决定**：正常推进业主大会，由全体业主表决物业去留。
-- **会议未达成一致**：业主大会是否能在诉讼期间召开、物业去留、小区问题整改责任归属均未达成一致。
-## 行动项与分工
-- **物业方**：本月内完成起诉手续，集团法务今日操作。
-- **业主方**：正常推进业主大会召开流程。
+- **物业方决定**：本月正式起诉业委会，以阻碍正常经营、造成经济损失为由，已与集团法务及法院沟通。
+- **业主方决定**：正常推进业主大会，表决物业去留；若物业起诉将反诉。
+- **会议结果**：双方未达成一致，矛盾激化，无实质调解结果。
 ## 待确认与风险
-- **业主大会程序**：物业方称起诉期间无法更换物业公司，业主方认为无法律依据阻止召开，未达成一致。
-- **欠费与整改死循环**：物业称欠费170多万导致无力整改，业主称整改不到位不愿缴费，矛盾持续。
-- **监控数据缺失**：业主称上月进贼时警方未能从监控获取数据，存在安全隐患。
-- **围墙缺口**：业主称北边围墙缺口可随意进出，物业称属红线外违建、无处理义务。
-- **雨水倒灌**：业主称明年再有大雨可能再次造成财产损失。
-- **地产破产**：物业称地产公司已申请破产，配套维修与补亏款无法追讨。</t>
+- **业主大会合法性**：物业方称诉讼期间无法更换物业公司，业主方质疑该说法并称将咨询律师，业主大会能否在诉讼期间召开未定。
+- **物业费与服务先后**：物业方要求先回款再维修，业主方认为服务无滞后性、必须先正常服务，双方未达成一致。
+- **安全风险**：监控几乎全部损坏、围墙缺口导致社会人员随意进出，存在安全隐患。
+- **财产风险**：雨水倒灌自2019年未解决，明年大雨可能再次造成财产损失。
+- **恶性循环风险**：物业费欠费导致服务恶化，服务恶化又加剧欠费，形成恶性循环。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>68.3</v>
+        <v>60.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/4595</t>
+          <t>21511/4624</t>
         </is>
       </c>
     </row>
@@ -2419,95 +2428,90 @@
       <c r="C6" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌论坛以「具身智能」为主题，由发言者2担任主持人，汇聚了来自学术界的老师、博士生以及业界嘉宾，围绕具身智能领域的关键技术问题与发展趋势展开研讨，旨在促进学术与产业交流。讨论覆盖了具身形态与硬件期待、世界模型的定义与构建、强化学习与模仿学习的路线之争、数据采集与仿真数据的作用，以及产业投资视角下的发展预测等多个核心议题。
-- **具身智能的形态与硬件期待**：探讨具身智能最终会收敛为何种形态（人形机器人或特种机器人），以及现有硬件能否支撑大规模真机评估与算法迭代。
-- **世界模型的定义与构建**：厘清强化学习领域与计算机视觉领域对世界模型概念的不同理解，以及世界模型是否需要3D归纳偏置。
-- **强化学习与模仿学习的路线之争**：讨论未来策略学习的最终路线，是单独采用模仿学习或强化学习，还是两者融合。
-- **数据采集与仿真数据的作用**：探讨真机数据与仿真数据的成本与价值，以及如何高效、低成本地获取高质量数据。
-- **产业投资视角下的具身智能发展**：分析具身智能赛道的融资规模、发展阶段与未来市场空间。
+本次圆桌论坛由具身智能领域多位嘉宾与博士生参与，围绕具身智能的技术路线、数据策略与产业前景展开研讨。与会者包括来自多模态大模型与具身智能融合、强化学习、数据采集与柔性物体操作、具身模型与世界模型等方向的博士生，以及来自学术界与产业界的嘉宾。论坛旨在通过学术与产业观点的碰撞，探讨具身智能发展的关键问题与未来方向，覆盖具身形态与硬件期待、世界模型定义、强化学习与模仿学习路线、数据采集与仿真数据作用、产业投资前景等议题。
+- **具身智能的形态与硬件期待**：探讨具身智能最终收敛为何种形态（人形机器人或特种机器人），以及硬件应如何支撑大规模真机评估与算法部署。
+- **世界模型的定义与分歧**：讨论强化学习领域与计算机视觉领域对世界模型的不同理解，以及世界模型是否需要三维归纳偏置、是否应统一为单一模型。
+- **强化学习与模仿学习的路线之争**：探讨未来策略学习的最终路线，是单独采用强化学习或模仿学习，还是两者融合，以及如何融合。
+- **数据采集与仿真数据的作用**：讨论真实数据、仿真数据与无标注数据的优先级与比例，以及如何保证数据质量、实现规模化采集。
+- **产业投资视角下的具身智能发展**：分析具身智能作为潜在万亿级市场的融资规模、未来波次与产业变革对技术形态的影响。
 # 核心观点
 ## 具身形态与硬件期待
-- **发言者3（机械领域视角）**：从机械与传感器角度反问具身形态最终收敛为何——人形机器人、科幻片中可变形的方块，还是机械领域所谈的「机械智能」（如软手通过强摩擦和顺应性在较大误差下仍能抓牢物体）；并期待算法/软件方向对硬件学科提出需求。
-- **发言者4（博士生）**：硬件需高寿命、高可靠性；训练VLA并大规模真机评估时，模型预测撞桌子等失误会使机器人损坏，难以可靠scale up；现有工业机械臂并非为此设计，需要个人柔顺的硬件结构以支持更大规模的真机评估。
-- **发言者2（主持人）**：具身智能一定是软硬件协同优化的范式；以松灵产品为例，第二代在遥操和策略部署上明显优于第一代；与任老师合作的凝胶夹爪可反馈触觉、更稳且摩擦力更好，体现协同进化。
-- **发言者5（老师）**：若大模型从最上直通最下，会消除硬件迭代的可能性——新硬件（如软体机器人）出现时前端大模型需完全重新训练；以人手断后大脑仍能工作为例，主张至少分两层：大脑不变，小脑adaptive到肢体，软体部分的控制dynamics相应变化。
-- **发言者6（老师）**：从第一性原理出发，现实中桌椅等均为人设计，人形机器人（双足或轮式、带灵巧手）会占很大比例；但特种机器人（如车厂、微电子制造厂中实现97%以上自动化的机械臂）也大量存在，两类将并存。
-## 世界模型的定义与构建
-- **发言者8（博士生，强化学习视角）**：世界模型概念可追溯至1990-91年Sutton的Dyna-Q文章，定义为黑盒、输出下一时刻观测；2018年Schmidhuber和LeCun的定义包含表征（压缩到隐空间）与转移两个组件；强化学习领域的第一要义是**可交互**（最终目的是学策略），其次希望有好的物理规律体现，最后才引入3D或触觉等多模态信息。
-- **发言者7（老师，CV视角）**：CV界追求动态重建物理世界，可作为RL世界模型的工具，但目前仍不成熟；RL与CV关注点略不同——一个更端到端，一个更关注解耦表征，这是学术发展阶段导致的现状；提出「data vs inductive bias trade-off」的第一性原理：数据多时需要的inductive bias少，数据少时需要的多；以朱松纯学派与ImageNet、以及UniSim需要3D inductive bias为例，认为学术发展呈螺旋前进，最终由数据决定。
-- **发言者5（老师）**：以游戏主角跳楼与物理世界cosplay同一动作结局不同为例，认为世界模型可能无法统一——相同观测对应不同dynamics是歧义问题，一个世界模型难以同时acquire两个dynamics；但policy有可能统一（同一玩家可在游戏中跳楼、在现实中避免），故世界模型应是多个，policy可能是一个。
-- **发言者9（老师，反对意见）**：强化学习的世界模型是任务导向的——目标只是更好地学策略，最终只需latent state或reward，不一定需要CV那样复杂的模型；对发言者5的「统一模型」观点提出反例：不同物理结构可共享统一表征，是否仍算统一模型；发言者5回应称这相当于在模型中加condition（game or true），从可实现角度M个独立模型比一个高维可控condition模型更简单，且目前没有能建模所有Atari game的单一世界模型。
+- **发言者3（机械领域）**：将问题反弹给与会者——具身智能的“身体”最终会收敛成什么形态？是人形机器人，还是像《星际穿越》中可变形的大方块那样的非人形态；机械领域有“机械智能”思路，如软手靠强摩擦与顺应性，在抓取误差较大时也能抓牢，希望了解算法与软件视角对硬件学科的期待。
+- **发言者4（博士生）**：对硬件提出寿命与可靠性要求——训练VLA需大规模真机评估，模型预测撞桌子等行为几次就会损坏设备，难以可靠scale up；现有工业机械臂并非为此设计，需要个人柔顺的硬件结构以支持规模化真机评估。
+- **发言者2（主持人）**：主张具身是软硬件协同优化的范式——以松灵产品两代迭代为例，第二代在遥操与策略部署上明显优于第一代；与任老师合作发现加凝胶的夹爪可反馈触觉且摩擦力更好，抓取更稳，体现协同进化。
+- **发言者5**：反对大模型从最上直通最下的单一形态——若新硬件（如软体机器人）出现，前端大模型可能需完全重新训练；以手断后大脑仍能指挥右手泡咖啡为例，认为至少应分大脑与小脑两层，大脑不变，小脑adaptive到肢体，软体部分的控制dynamics相应变化。
+- **发言者6**：从第一性原理出发预测形态——现实中桌椅皆为人设计，必有一类人形机器人（双足或轮式，带灵巧手），引马斯克采访称其公司花一半精力做22自由度灵巧手；同时特种机器人在车厂、微电子制造厂已实现97%以上自动化，人形与特种机器人将长期并存。
+## 世界模型的定义与分歧
+- **发言者8（博士生）**：从强化学习视角定义世界模型——概念可追溯至1990-91年Sutton的Dyna-Q文章，本质是黑盒，输入当前观测与action，输出下一时刻观测，第一要义是**可交互**（最终目的是学策略）；2018年Schmidhuber与杨立昆定义的世界模型含表征与转移两个组件；当前世界模型在物理规律体现上欠缺明显，希望引入3D信息、触觉等多模态进一步完善。
+- **发言者7**：CV界共识是世界模型即动态重建物理世界，可作为RL世界模型的工具；但三维计算机视觉技术栈深，RL博士生难以完整学习，导致RL领域不太关注三维表征——这是学术发展阶段导致的现状；提出**数据规模与inductive bias的权衡**：数据多时需要的inductive bias少，数据少时需要的多，GPT与ImageNet的成功说明大规模学习可不需要inductive bias，而UniSim等新模型又需要3D inductive bias，学术发展呈螺旋前进状态。
+- **发言者5**：以《刺客信条》主角跳楼与真人cosplay同一动作却结局不同为例，认为世界模型面对相同观测却需不同输出，是**完全歧义的问题**，单一世界模型无法同时建模两个dynamics；但policy可以统一——人既能玩游戏也能在真实世界避免跳楼，是同一个大脑同一个policy；结论是世界模型可能做不到统一，policy有可能做到。
+- **发言者9**：提出反对意见——CV世界模型带3D inductive bias并不必然更好；强化学习的世界模型是**任务导向**的，目标只是更好学策略，最终只需latent state或reward，不一定需要CV式完整重建；针对发言者5的歧义论证，提出不同物理结构可共享统一表征，即“在world model上加一个condition（是游戏还是真实）”，但发言者5回应称M个独立模型比一个高维可控condition模型更简单，且目前没有单一world model能建模所有Atari游戏，用GPT回归大概率是强记。
 ## 强化学习与模仿学习的路线之争
-- **发言者2（主持人）**：派零团队在收集上千至近万小时数据后仍明显看到模仿学习的瓶颈，并非scale后性能如预期提升；语言模型最终靠RLHF调整，o1引入后思维链与MCTS被广泛熟知；未来落地不一定是IL与RL割裂，可能有先模仿学习pretrain再RL精调、或IL作为RL数据收集部分等方案。
-- **发言者10（业界嘉宾）**：公司采用模型强化加机理融合方式；监督学习在具身任务中动作空间大、数据分布远不足以覆盖高维动作；纯强化学习强依赖仿真环境，sim-to-real迁移困难；实物强化学习需严格限定决策规模与任务设定（如分层：上层RL做决策，底层用MPC或DWA等传统方法执行），直接学从上到下到电流的控制依然困难。
-- **发言者9（老师）**：不认为收敛到最后强化或模仿能单独完成，较好解是混合方式；底层如PID等传统方法能解决的无需从scratch替代；复杂问题（AlphaStar、GPT）都是先模仿后强化，from scratch跑强化样本复杂度不可接受，模仿提供的先验信息没有坏处；单独模仿无法达到专家水平（除非任务就是模仿专家），单独强化也不行（除非任务足够简单）。
-- **发言者5（老师）**：PID能做的系统必然有反馈，没有反馈做不了控制，因此可完全拿该反馈作为强化学习执行过程中的reward；过去用PID效果不够好，现在通过强化可做得更好。
-- **发言者11（老师）**：模仿学习与强化学习并无本质冲突，只是获取运动先验的不同方式——有现成数据可用imitation learning，没有（如人类复杂运动数据）可用RL（如DeepMind的mimic）先获取，再建模latent；有了latent后可用RL快速找到对应latent完成任务。
+- **发言者10（业界）**：公司采用**模型强化加机理融合**——监督学习动作空间大，数据分布远不足以覆盖高维动作；纯强化学习强依赖仿真环境，sim-to-real迁移困难；实物强化学习需严格限制决策规模与任务设定，若将state-action对限定好，上层用强化学习做决策、底层用MPC或DWA等传统方法执行，可提升整体性能；这是实际部署经验得出的结论，偏工程视角。
+- **发言者9**：基本同意发言者10，但不同意“收敛到最后强化或模仿能单独完成”——复杂任务应**先模仿后强化**；底层PID等传统方法能解决的无需从scratch重做；从历史看AlphaStar、GPT等复杂问题都是先模仿后强化，from scratch跑强化样本复杂度不可接受；模仿提供先验信息无坏处，工程手段可解决“先模仿再强化会不好”的学术争议；单独模仿无法达到专家水平（除非任务就是模仿专家），单独强化也不行（除非任务足够简单）。
+- **发言者5**：回应真机reward获取问题——PID能做的系统必然有反馈，没有反馈做不了控制，因此可完全拿这个反馈作为强化学习的reward；过去用PID效果不够好，现在用强化可做得更好，但PID能做说明强化必然走得成。
+- **发言者11**：认为IL与RL并无本质冲突——学人类运动先验可用DeepMind的强化学习优化（如mimic），也可用模仿学习；目标是获得运动先验的latent，有现成数据就用模仿学习，没有就用强化学习生成，再通过RL快速找到对应latent完成任务；具体用哪种取决于数据可用性。
 ## 数据采集与仿真数据的作用
-- **发言者11（老师，真机数据派）**：视角控制对policy表现影响大，采集时严格控视角与标定；手眼标定看似已解决但至今仍有人在发文章、解决得不好；Open X等数据集只捕捉本体信息（末端、关节角度、力矩），缺少物体运动信息，其团队采集时一定记录物体运动（当时设备有限只能采刚体和关节体）。
-- **发言者4（博士生，真机数据派）**：all in reward采集路线；柔性体操作（叠衣服、系鞋带、拉拉链）现有仿真需IPC等先进图形学技术，算力要求高且掌握的人少（如UCLA蒋正凡老师），进展缓慢；真实世界是最好的仿真器，reward采集相对低成本；终极采集形态可能是脑机接口或机电方式，无感、多模态、触觉力觉视觉内生，现阶段可穿戴设备是可行方案；互联网视频数据与机器人所需数据差异大——网上叠衣服视频都是平整状态，而机器人面对的是从洗衣机取出揉成一团的状态，人类习以为常的简单事恰恰是机器人最缺的数据。
-- **发言者2（主持人，仿真数据派）**：互联网数据在数据金字塔最底层、质量低（本人洗ego4d数据集洗了三个月）；仿真数据可给任意初始状态收集数据，sim-to-real概括较大；实验结果显示300条仿真数据加20条真机数据即可显著提升成功率（用很原始的finetune方法）；仿真与真机数据并不相斥，海量仿真数据（随机位置、orientation、初始状态）配几十条真机数据可训出较好policy；柔性体仿真并非解决不了，而是图形学领域认为机器人布料模拟不够格发顶会、机器人领域又不懂计算，未来可能有发展。
-- **发言者7（老师）**：用真实还是仿真数据case by case看成本；室内服务机器人真机数据收集有可行性，但自动驾驶corner case让真人去「鬼探头」太危险；主张加入第三域——**无标注真实数据**，2025年应在自动驾驶和具身智能领域推广大规模利用无标注数据（如segment anything、depth anything），不再讨论1:9、2:8、5:5这类有标注数据配比问题。
-- **发言者7（老师，国产仿真系统）**：国产仿真系统是产业问题，有公司（如宋应）赌会被卡脖子而做国产替代，business by business是很好的生意；技术上最终会比较统一，但business上很复杂，取决于是否脱钩卡脖子。
+- **发言者11**：数据质量关键在于**视角控制与标定**——Open X等数据集融合多家数据，相机视角无法固定（有的放末端、有的放本体外），视角非常影响policy表现；手眼标定看似已解决但至今仍有人在发文章；Open X等数据集只捕捉本体信息（末端、关节角度、力矩），缺少物体运动信息，其团队采集时记录刚体和关节体的物理变化，随技术进步数据质量会提高。
+- **发言者4（博士生）**：all in真实数据采集路线——柔性体操作（叠衣服、系鞋带、拉拉链）现有仿真需IPC等先进图形学技术，算力要求高且掌握者少（如UCLA蒋正凡老师），进展慢；真实数据是相对低成本方案，“大自然就是最好的仿真器”；终极采集形态可能是脑机接口或机电方式，无感采集多模态数据，现阶段可穿戴设备是可行方案；互联网视频数据与机器人所需数据差异大——网上教叠衣服的视频都是平铺状态，但机器人见到的是从洗衣机取出揉成一团的状态，人类习以为常的简单事恰恰是机器人最缺的数据。
+- **发言者2（主持人）**：仿真数据与真实数据**并非相斥**——用仿真生成300条数据训策略直接真机测成功率很低，但300条仿真数据加20条真机数据成功率显著提升，且用的是很原始的finetune方法；仿真数据可提供海量随机位置、orientation与初始状态，配合少量真机数据可训出较好policy；互联网数据质量低，本人受Ego4D数据集“毒害”，清洗耗时三个月，大量数据与训练有效policy无关，处于数据金字塔最底层。
+- **发言者7**：真实数据与仿真数据选择应**case by case看成本**——室内服务机器人真机数据收集有可行性，但自动驾驶corner case让真人去“鬼探头”太危险；提议2025年加入第三个domain——**无标注真实数据**，像Segment Anything、Depth Anything那样大规模利用无标注数据，将成为2025年的主题；对国产仿真系统，认为有人（如宋应团队）赌会被卡脖子而做国产替代，business上很复杂，技术上最终会统一。
 ## 产业投资视角下的具身智能发展
-- **发言者7（老师）**：具身智能被认为是手机和汽车之后的第三个万亿级市场，这是资本投入的原因；当前10亿人民币融资规模相比自动驾驶、大模型、互联网都很小（互联网时代美团、滴滴融资规模大得多），规模小是因为行业还非常早；资本界基本认为过完年后具身智能融资会开始变冷、进入低谷，之后预测有四波：第二波达自动驾驶融资规模、第三波达大模型规模、第四波达互联网规模，何时到来取决于技术突破；这三四波技术变革导致的产业变革会深刻改变具身大模型的硬件和云端模型形态，暂时无法预测。
+- **发言者7**：具身智能被视为**手机和汽车之后的第三个万亿级市场**——10亿人民币融资相比整个市场cap很少，相比自动驾驶、大模型、互联网的融资规模逐级更小，规模小是因为行业还非常早；资本界预测过年后具身智能融资将转冷进入低谷，之后会有多波增长：第2波接近自动驾驶融资规模，第3波接近大模型，第4波接近互联网；未来3-4波技术变革将深刻改变具身大模型硬件与云端模型形态，目前无法预测。
 # 达成共识与解决方案
-**未形成统一结论**。本场围绕具身智能形态、世界模型构建、策略学习路线与数据采集方式四个议题展开讨论，各方观点存在明显分歧，但形成了若干倾向性认识与主流意见。
+**未形成统一结论**。本场讨论围绕具身智能的形态与硬件、世界模型、策略学习路线、数据策略等议题展开，各方观点存在明显分歧，但形成了若干倾向性认识与主流意见。
+## 具身形态与硬件
+- **倾向性认识**：具身智能是**软硬件协同优化的范式**，硬件迭代与算法进步相互促进（发言者2以松灵产品两代迭代为例，说明第二代在遥操与策略部署上优于第一代；夹爪加凝胶后可反馈触觉、增加摩擦力与稳定性）。
+- **倾向性认识**：大模型不应从最上直通最下，**至少应分大脑与小脑两层**——大脑保持稳定，小脑需自适应肢体变化（发言者5以人手断后大脑仍能工作、底层控制需重新适应为例）。
+- **倾向性认识**：**人形机器人与特种机器人将长期并存**——人形机器人因现实环境为人设计而存在，特种机器人在工业制造中已实现97%以上自动化（发言者6）。
+- **硬件需求共识**：发言者4提出硬件需高寿命、高可靠性，现有工业机械臂并非为大规模真机评估设计，需要个人柔顺的硬件结构以支持scale up的评估；发言者2与发言者4均认可硬件需配合算法迭代改进。
+## 世界模型
+- **倾向性认识**：强化学习领域的世界模型概念可追溯至1990-91年Dyna-Q，**首要要素是可交互**，最终目的是学策略；CV界世界模型共识是动态重建物理世界，可作为RL世界模型的工具（发言者8、发言者7）。
+- **倾向性认识**：世界模型是否需要三维inductive bias**由数据规模决定**——数据少时需要的inductive bias更多，数据多时更端到端的方式更好（发言者7）。
+- **倾向性认识**：**世界模型可能无法统一为单一模型**（因存在歧义问题），但策略有可能统一——人可同时适应游戏与真实世界（发言者5）；发言者9提出不同物理结构可能共享统一表征，但发言者5认为将M个独立世界模型装入一个高维可控条件模型，从可实现角度M个模型更简单。
+- **倾向性认识**：强化学习的世界模型是**任务导向的**，CV世界模型做得足够好可用于强化，但为解强化任务是否需要CV式世界模型存疑（发言者9）。
+## 策略学习路线
+- **倾向性认识**：**复杂任务应先模仿学习后强化学习**，单独模仿或单独强化均不可行——模仿提供好的先验信息，强化用于超越专家水平（发言者9）；发言者10表示公司实际采用模型强化加机理融合方式。
+- **倾向性认识**：监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境、sim-to-real迁移困难，需限制决策空间与任务设定（发言者10）。
+- **倾向性认识**：IL与RL并非本质冲突，运动先验可通过模仿或强化获取，具体取决于数据可用性（发言者11）。
+- **倾向性认识**：PID能做的系统必有反馈，**该反馈可作为强化学习的reward**（发言者5）。
+## 数据采集与仿真
+- **倾向性认识**：**仿真数据与真实数据结合有效**——300条仿真数据加20条真机数据可显著提升成功率（发言者2，基于其团队实验结果）。
+- **倾向性认识**：真实数据与仿真数据的选择应**case by case看成本**（发言者7）。
+- **倾向性认识**：数据采集中**视角控制与标定至关重要**，Open X等数据集视角不固定影响模型表现，且缺少物体运动信息（发言者11）。
+- **倾向性认识**：真实数据是低成本方案，仿真技术对柔性物体模拟算力要求高且进展慢；终极数据采集形态可能是脑机接口或机电方式，现阶段可穿戴设备是可行方案（发言者4）。
+- **倾向性认识**：互联网数据质量低，与机器人所需数据差异大——如Ego4D数据集清洗耗时三个月，大量数据与有效策略训练无关（发言者2）；互联网视频中叠衣服教程多为平铺状态，缺少从混乱状态展平的数据（发言者4）。
+- **倾向性认识**：**2025年应推广大规模利用无标注数据**，如segment anything和depth anything模式（发言者7）。
+## 解决方案
+- **策略学习方案**：采用**先模仿学习预训练、再强化学习微调**的混合路线，底层可用传统方法（如MPC、DWA等）执行，上层由强化学习做决策（发言者10、发言者9）。
+- **数据采集方案**：采集时严格控制相机视角并做好标定，记录物体运动信息（刚体与关节体物理变化）（发言者11）。
+- **数据结合方案**：对单一任务采集海量仿真数据（覆盖物体随机位置、随机orientation、任意初始状态），配合少量真机数据（约20条）联合训练策略（发言者2）。
+- **数据规模化方案**：通过可穿戴式设备在日常活动中无感采集多模态数据，而非仅靠雇佣人员批量采集（发言者4）。
+# 未决分歧与后续探索
 ## 具身形态与硬件期待
-- **倾向性认识**：发言者6认为**人形机器人与特种机器人将长期并存**——现实中的桌椅等设施按人体尺寸设计，人形机器人会占很大比例（双足或轮式，配灵巧手）；同时车厂、微电子制造厂已有大量特种机械臂实现97%以上自动化，特种机器人也大量存在于工业生产中。
-- **倾向性认识**：发言者5提出**大模型不应从最上直通最下，至少应分两层**——大脑不随肢体变化而更换，小脑需自适应肢体变化；以手断后仍能用另一只手泡咖啡为例，底层控制模型（小脑）应随身体惯量、动力学变化而调整，大脑保持不变。
-- **倾向性认识**：发言者2主张**具身智能是软硬件协同优化的范式**——以松灵产品两代迭代为例，第二代在遥操与策略部署上明显优于第一代；与任老师合作的凝胶夹爪可反馈触觉、抓取更稳且摩擦力更好，体现软硬件协同进化。
-- **倾向性认识**：发言者4提出硬件需**高寿命、高可靠性**——训练VLA需大规模真机评估，机器人易因模型预测撞桌等行为损坏，现有工业机械臂并非为此设计；需要个人柔顺的硬件结构以支持规模化评估。
-## 世界模型的定义与构建
-- **倾向性认识**：发言者7认为**CV界追求重建物理世界的目标可作为RL世界模型的工具**，但当前仍不成熟；CV与RL领域关注点不同——RL更端到端，CV更关注解耦表征，这是学术发展阶段导致的现状。
-- **倾向性认识**：发言者7提出**数据规模决定inductive bias需求**——数据多时需要的inductive bias少，数据少时需要的多；以ImageNet、GPT的成功说明大规模学习可减少inductive bias，而UniSim等新模型因数据不足仍需3D inductive bias。
-- **倾向性认识**：发言者5认为**世界模型可能无法统一，但policy有可能统一**——同一输入对应不同动力学输出（游戏中跳楼安全落地、现实中跳楼死亡）是歧义问题，一个世界模型难以同时建模；但同一policy可同时应对游戏与现实场景。
-- **倾向性认识**：发言者9认为**强化学习的世界模型是任务导向的**——目标是更好学策略，只需产生latent state或reward即可，不一定需要CV那样复杂的3D重建模型。
+- **人形与特种机器人并存与否**：发言者6预测人形机器人（双足或轮式，带灵巧手）与特种机器人将长期并存，理由是现实环境为人设计、特种机器人在车厂和微电子制造厂已实现97%以上自动化；发言者3从机械领域提出具身形态收敛问题（人形还是可变形方块），未获直接回应，双方未达成一致。
+- **大模型是否应贯通硬件层**：发言者5主张模型不应从最上直通最下，至少分大脑与小脑两层——大脑不变、小脑adaptive到肢体（以手断后大脑仍能指挥右手泡咖啡为例）；发言者6认为当前多模态大模型微调方案不是终极形态，世界模型可能更接近人脑水平但也不一定是最终方案，最终可能需全新网络架构。分歧点在于模型分层还是贯通，需验证何种架构能适应硬件迭代。
+- **硬件寿命与可靠性要求**：发言者4提出具身智能训练中大规模真机评估时机器人易因预测撞桌等损坏，现有工业机械臂非为此设计，需个人柔顺硬件结构以支持scale up的评估；发言者2以松灵两代产品迭代说明硬件提升改善遥操与策略部署，并提到加凝胶夹爪可反馈触觉、摩擦力更好。分歧点在于硬件应优先满足可靠性还是协同进化，发言者4未获明确回应。
+## 世界模型的定义与分歧
+- **强化学习与CV世界模型是否同一概念**：发言者8指出RL领域世界模型概念可追溯至1990-91年Dyna-Q，第一要义是可交互（黑盒输入输出下一时刻观测），其次需物理规律，最后才引入3D等模态；发言者7认为CV界共识是动态重建物理世界，可作为RL世界模型的工具，但RL与CV关注点略不一样——一个更端到端、一个更解耦表征。发言者9进一步主张RL世界模型是任务导向的，只要有助于学策略即可，CV式世界模型并非必要。分歧点在于RL是否需要CV式三维重建世界模型，发言者9与发言者8持任务导向立场，发言者7持工具论立场。
+- **世界模型能否统一为单一模型**：发言者5以游戏与真实世界相同观测不同结局为例，认为世界模型因歧义问题无法统一，但policy可能统一（同一大脑可同时适应游戏与真实世界）；发言者9提出反例——不同物理结构可共享统一表征，或给世界模型加condition（区分游戏/真实），发言者5回应加condition会使模型维度极高、可实现性差，M个独立模型更简单，且目前没有单一世界模型能建模所有atari游戏。分歧点在于统一模型还是分立模型，发言者9承认同意发言者5观点，仅基于其例子找反例。
+- **世界模型是否需要三维inductive bias**：发言者7提出数据规模与inductive bias的权衡——数据多时inductive bias需求减少、端到端方式更好，数据少时需更多inductive bias（如UniSim需occupancy生成），并称梦想写一篇data bias trade off的paper；发言者9认为CV世界模型带三维inductive bias不一定更好，RL世界模型（如dreamer）不带voxel、光照纹理材质。分歧点在于三维inductive bias的必要性，发言者7认为由数据量决定、拭目以待，发言者9持保留态度。
 ## 强化学习与模仿学习的路线之争
-- **倾向性认识**：发言者9主张**复杂任务应先模仿再强化**——单独模仿无法达到专家水平（除非任务本身就是模仿专家行为），单独强化样本复杂度不可接受；以AlphaStar、GPT为例，先模仿提供好的先验信息，再强化优化至超越专家水平。
-- **倾向性认识**：发言者10从产业实践角度主张**模型强化加机理融合**——监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境、sim-to-real迁移困难；需将强化学习的决策空间与任务设定限制好，上层用强化学习做决策，底层用MPC、DWA等传统方法执行。
-- **倾向性认识**：发言者5提出**PID能做的系统必有反馈，反馈可作为强化学习的奖励**——控制领域天然存在反馈机制，过去用PID效果不够好，现在通过强化可做得更好。
-- **倾向性认识**：发言者11认为**模仿学习与强化学习并无本质冲突**——两者只是获取运动先验的不同方式：有现成数据可用模仿学习，没有数据（如人类复杂运动）可用强化学习先获取，再以BC形式建模latent，后续任务用RL快速找到对应latent完成。
+- **最终路线是融合还是单一方法**：发言者10表示公司采用模型强化加机理融合，因监督学习动作空间大、数据分布远不足以覆盖高维动作，纯强化学习强依赖仿真环境、sim-to-real迁移困难，需限制决策空间与任务设定（如上层强化做决策、底层用MPC或DWA等传统方法）；发言者9认为复杂任务应先模仿后强化，单独模仿到不了专家水平（除非任务就是模仿专家），单独强化from scratch样本复杂度不可接受（以AlphaStar、GPT为例），并认为「先模仿再强化会不好」的学术宣称可用工程手段解决；发言者11认为IL与RL并无本质冲突——运动先验有数据可用模仿学习获取、无数据可用强化学习（如DeepMind的mimic）生成，再建模latent完成具体任务。分歧点在于是否融合及融合方式，发言者10与发言者9主张融合，发言者11认为两者不冲突、视数据可用性而定。
+- **真机强化学习的reward获取**：发言者2提出真机复杂任务中reward如何获取的问题——仿真有上帝视角，真机detection和传感器有偏差；发言者5回应PID能做的系统必有反馈，反馈可直接作为强化学习的reward，过去用PID效果不够好、现在用强化做得更好。分歧点在于真机reward来源是否可靠，发言者5主张反馈即reward，发言者2未明确回应是否认可。
 ## 数据采集与仿真数据的作用
-- **倾向性认识**：发言者2分享**仿真数据与真机数据结合可显著提升成功率**——300条仿真数据训完策略直接真机测试成功率很低，但加上20条左右真机数据微调后成功率显著提升；仿真数据可提供物体随机位置、随机朝向、任意初始状态的海量覆盖。
-- **倾向性认识**：发言者4主张**真实世界是最好的仿真器**——柔性体操作（叠衣服、系鞋带）现有仿真需IPC等先进图形学技术，算力要求高且掌握者少；真机数据采集相对低成本，且生活中场景丰富。
-- **倾向性认识**：发言者4提出**可穿戴设备是现阶段可扩展的数据采集方案**——终极形态可能是脑机接口或机电方式，无感采集多模态数据；现阶段通过可穿戴设备在人们日常做事过程中采集数据，比雇佣人员一波波采集更可扩展。
-- **倾向性认识**：发言者11强调**数据质量关键在于视角控制与标定**——Open X等数据集融合多家数据、相机视角无法固定，而视角对policy表现影响大；其团队采集时严格控制视角并记录物体运动（刚体与关节体），弥补Open X等数据集只捕捉本体信息、缺少物体运动的不足。
-- **倾向性认识**：发言者7提出**2025年应推广大规模利用无标注真实数据**——不再讨论有标注真实数据与仿真数据的比例（1:9、2:8、5:5等），应像Segment Anything、Depth Anything那样，在自动驾驶和具身智能领域大规模利用无标注数据。
-- **倾向性认识**：发言者4指出**互联网视频数据与机器人所需数据差异大**——网上叠衣服视频多为平整状态的教学，而机器人需处理从洗衣机取出揉成一团的状态；人类习以为常的简单任务恰是机器人最缺的数据，需补上这一环节。
-# 未决分歧与后续探索
-## 具身形态与硬件路线
-- **具身最终形态**：发言者3提出具身身体会收敛成什么样子，是人形机器人还是科幻片中可变形的大方块；发言者6认为从第一性原理出发，现实中桌子椅子都为人设计，人形机器人（双足或轮式、带灵巧手）会占很大比例，但特种机器人也大量存在于工业生产制造中（如车厂、微电子制造厂已有97%以上自动化用机械臂），两者将并存；发言者7从产业角度预测未来3-4波技术变革会深刻改变本体形态，但暂时无法预测。
-- **大模型与硬件是否应一体化**：发言者5主张大模型不应从最上直通最下，至少应分两个层面——大脑不变、小脑自适应肢体变化，并举手断后大脑仍能工作、底层控制需适应新dynamics为例；发言者6认为当前多模态大模型微调到机器人任务不是终极方案，世界模型可能更接近人脑水平，但可能也不是最终形态，最终可能需要全新网络架构。
-- **硬件寿命与可靠性**：发言者4提出具身智能实验特别是训练VLA和真机大规模evaluation时，机器人容易因模型预测撞桌子等损坏，现有工业机械臂并非为此设计，需要个人柔顺的硬件结构支持scale up的evaluation。
-- **软硬件协同优化**：发言者2认为具身一定是软硬件协同优化的范式，举例松灵第二代产品在遥操和策略部署上比第一代好很多；与任老师学术合作发现加凝胶的夹爪可反馈触觉、更稳且摩擦力更好。
-## 世界模型的定义与构建
-- **世界模型概念溯源**：发言者8指出世界模型概念可追溯至1990-91年Sutton的Dyna-Q文章，定义为黑盒、输出下一时刻观测；2018年Schmidhuber和LeCun定义的世界模型包含表征和转移两个组件——表征把视觉等模态压缩到隐空间，转移是在隐空间下由当前观测和action预测变化。
-- **RL与CV对世界模型的理解差异**：发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，但三维计算机视觉技术栈深，RL博士生难以完全学习，导致RL领域不太关注三维表征；发言者8从强化学习角度认为世界模型第一要义是可交互（最终目的是学策略），其次是物理规律体现，最后才是引入3D信息或触觉等多模态感知；发言者9认为强化学习的世界模型是任务导向的，目标是更好学策略，不一定需要CV那样复杂的模型。
-- **世界模型是否需要3D inductive bias**：发言者7提出数据规模与inductive bias的权衡——数据多时需要的inductive bias变少，数据少时需要更多；以UniSim为例，在NeRF上做需要3D inductive bias，但未来数据scaling up后可能不需要，更端到端的方式会更好；发言者9提出反对意见，认为不能简单用inductive bias区分RL和CV的世界模型。
-- **世界模型能否统一**：发言者5以游戏主角跳楼在游戏和物理世界结局不同为例，认为世界模型可能无法统一（相同输入不同输出是歧义问题），但policy有可能统一——人可以在游戏中跳楼而在真实世界避免，同一个大脑同一个policy；发言者9提出反例：是否可以在世界模型中加入condition（区分游戏或真实），发言者5回应从可实现角度M个独立模型比一个高维controllable condition模型更简单，且目前没有atari game能靠一个世界模型建模所有游戏。
-## 强化学习与模仿学习的路线之争
-- **模仿学习的瓶颈**：发言者2提到派零团队在收集上千小时近万小时数据后，仍明显看到基于模仿学习的瓶颈存在，scale之后性能提升并非如大家所想。
-- **产业界的融合路线**：发言者10介绍公司采用模型强化加机理融合方式，因监督学习数据分布远不足以覆盖高维动作空间，纯强化学习强依赖仿真环境、sim-to-real迁移困难；其强化PC工作做任务分层，上层强化学习做决策，底层用MPC或DWA等传统方法执行，整体框架性能有提升。
-- **先模仿后强化的路线**：发言者9认为复杂任务应先模仿再强化——单独模仿无法达到专家水平（除非任务就是模仿专家），单独强化from scratch样本复杂度不可接受；以AlphaStar和GPT为例，先模仿提供好的先验信息不会导致强化做不好，工程手段可解决。
-- **反馈机制与奖励获取**：发言者5回应真机复杂任务reward获取问题，认为PID能做的系统必然有反馈，可完全拿反馈作为强化学习执行过程中的reward，过去用PID效果不够好，现在通过强化做得更好。
-- **模仿与强化并非冲突**：发言者11认为两者没有本质冲突，只是获取运动先验的不同方式——有现成数据可从模仿学习角度做，没有数据可用DeepMind的仿真强化方式先获取，再通过RL找到对应latent完成任务。
-## 数据采集与仿真数据的作用
-- **数据质量与视角控制**：发言者11强调视角非常影响模型policy表现，采集时对视角控制很好；标定非常重要，手眼标定至今仍有人在发文章、解决得不太好；Open X等数据集融合多家数据、相机视角无法固定，且只捕捉本体信息（末端、关节角度、力矩），缺少物体运动信息，其团队采集时一定记录物体运动（当时设备有限只能采集刚体和关节体）。
-- **真实数据采集路线**：发言者4主张all in reward采集路线，认为真实世界是最好的仿真器，相比高性能仿真算法的高昂算力是更低成本方案；终极形态可能是脑机接口或机电方式，无感采集多模态数据（触觉、力觉、视觉、听觉内生），现阶段可穿戴设备是能scale的方案。
-- **互联网视频数据的局限**：发言者4指出互联网视频与机器人所需数据差异大——网上叠衣服视频都是平整状态开始教，但机器人见到的是从洗衣机拿出来揉成一团的状态，人类从小就会的常见事没人拍视频发网上，恰是机器人最缺的数据；发言者2分享ego4d数据集清洗三个月、大量数据与训练有效policy无关，互联网数据在数据金字塔最底层、质量较低。
-- **仿真数据与真机数据结合**：发言者2分享实验结果——300条仿真数据训完策略直接去real world测试成功率很低，但300条仿真数据加上20条少量真机数据，成功率有显著提升，且用的finetune方法非常原始（pretrain后真机数据快速finetune几次）。
-- **柔性体仿真进展缓慢**：发言者4指出柔性体操作（叠衣服、系鞋带、拉拉链）需要IPC等先进图形学技术，对算力要求高，全世界能做的人少（如UCLA蒋正凡做过高性能仿真技术），进展较慢；发言者2认为并非解决不了，而是做烟雾模拟的graphics研究者看不上机器人布料海绵模拟这个research方向。
-- **无标注真实数据作为第三域**：发言者7提出2025年应推广大规模利用无标注真实数据（如segment anything、depth anything），不要再讨论真实数据与仿真数据1:9、2:8、5:5的比例问题。
-- **国产仿真系统**：发言者2提问未来中国是否强依赖英伟达生态（Isaac Sim/Isaac Lab已开放柔性物体仿真接口）；发言者7回应国产仿真系统是产业问题，有公司（如宋应）赌会被卡脖子而做国产替代，business上会很复杂，技术上最后会比较统一。</t>
+- **真实数据与仿真数据的优先级与比例**：发言者4主张真实数据是低成本方案——柔性物体仿真需IPC等先进图形学技术、算力要求高且掌握者少（如UCLA蒋正凡夫），真实世界本身就是最好的仿真器；发言者2认为仿真数据与真实数据可结合——300条仿真数据加20条真机数据即可显著提升成功率（用较原始的finetune方法），但大量真机数据采集effort大；发言者7认为应case by case看成本——室内服务机器人真机数据可行，自动驾驶corner case让真人去鬼探头太危险。分歧点在于数据来源优先级与比例，发言者4主张真实数据为主，发言者2主张仿真与真实结合，发言者7主张按成本分场景，未达成共识。
+- **数据采集方式能否规模化**：发言者4提出终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴设备是可行方案，并指出互联网视频数据与机器人所需数据差异大——网上叠衣服视频都是平铺状态，机器人需要的是从洗衣机取出揉成一团的状态，这类常见任务无人拍视频上传；发言者2以Ego4D数据集清洗三个月为例说明互联网数据质量低、大量与有效策略训练无关。分歧点在于可穿戴设备采集的精度能否覆盖遥操数据，发言者2认为可穿戴设备精度上需cover gap才能走向好用，发言者4未获明确回应。
+- **是否发展国产仿真系统**：发言者2提出中国是否强依赖英伟达生态（Isaac Sim/Isaac Lab已开放柔性物体仿真接口）的问题，并留引子给发言者7；发言者7回应国产仿真系统产业问题复杂——有朋友宋应赌会被卡脖子而做国产替代，生意上会是很复杂的问题，技术上最后会比较统一，但工作人员不会直接touch这个生意。分歧点在于是否需国产替代，发言者2提出疑问，发言者7认为取决于脱钩与卡脖子风险，未深入讨论。
+- **无标注真实数据的利用**：发言者7提议2025年应在自动驾驶和具身智能领域推广大规模利用无标注真实数据（如segment anything、depth anything），认为讨论真实与仿真数据比例（1:9、2:8、5:5）是过时问题。此提议为发言者7个人主题，未获其他与会者明确回应。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>90.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/9241</t>
+          <t>21458/8734</t>
         </is>
       </c>
     </row>
@@ -3006,68 +3010,69 @@
       <c r="C7" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审，由最高人民法院组成合议庭公开开庭审理，审判长李少平，合议庭成员魏文超、黄年、王海峰、葛洪涛，法官助理张瑞。庭审围绕三个争议焦点展开：国开行是否善意取得抵押权、罚息复利计算及起算日期、东源煤电与东源煤业是否应连带给付违约金。各方充分发表辩论意见后，合议庭休庭评议并提出调解方案，各方均无异议，合议庭予以确认并出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案二审，由最高人民法院依法组成合议庭公开开庭审理，审判长李少平，合议庭成员魏文超、黄年、王海峰、葛洪涛。庭审围绕三个争议焦点展开：国开行是否尽到审查义务并善意取得抵押权、一审判决对罚息复息的计算及起算日期是否错误、东源煤电及东源煤业是否应连带给付违约金。各方充分发表辩论意见后，合议庭休庭评议并提出调解方案，各方当事人均无异议，合议庭予以确认，庭后出具调解书。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国家开发银行） | 请求撤销一审判决，改判支持其利息、罚息、复利及违约金主张；确认其对案涉设备享有抵押权。 | 主张已按人民银行规定查询融资租赁系统无登记，构成善意取得；利息计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；依合同第24条第3项主张千分之一违约金。 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决；认为国开行未在抵押时点查询系统，不构成善意；贷款提前到期应限期偿还；罚息不应作为复利基数；国开行未举证违约行为且未发函限期纠正，无权主张违约金。 | 主张2015年12月2日邮件已用红色标注设备名称一致，应引起国开行注意；合同约定限期偿还，当天要求偿还8.37亿本金不合理；罚息不能作为复利基数，有最高院判例支持。 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决；认为国开行未在抵押时点查询系统，不构成善意；主张对6项设备享有所有权。 | 主张国开行审查义务应扩展至东源煤电（借款人且与抵押人全资控股）；东源煤电出资行为系无权处分；案涉设备无唯一识别码，初始登记时未登记识别码。 |
-| 被上诉人（东源煤业） | 与东源煤电合并发表意见，请求驳回上诉。 | 委托共同代理人吴学成、李新海，与东源煤电意见一致。 |
+| 上诉人（国家开发银行） | 请求撤销一审判决相关判项，改判支持其利息、罚息、复利计算主张及违约金请求 | 主张已按央行规定查询融资租赁登记系统，审查义务仅限于抵押人曲靖电力公司，已尽审慎义务构成善意取得；利息应自2017年12月21日计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；依据合同第24条第3项主张千分之一违约金 |
+| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回国开行上诉请求，维持一审判决 | 主张国开行未尽注意义务，2015年12月2日邮件已用红色标注设备名称相同；宣布贷款提前到期未给合理期限，罚息不能作为复利基数；国开行未举证证明违反柜台前移和账户管理约定，未发纠正函无权主张违约金 |
+| 被上诉人（招银租赁） | 请求驳回国开行上诉请求，维持一审判决 | 主张国开行未在抵押时点查询融资租赁登记系统，不构成善意；东源煤电出资行为系无权处分，电力公司未取得设备所有权；招银租赁2012年已取得设备所有权 |
 # 举证与法庭调查
 ## 举证与质证
-- **国开行提交**：2018年9月对曲靖电力公司的融资租赁查询证书（第5组证据第1项），证明其已尽查询义务；东源方质证认为该查询证书不符合要求，依据2014年93号中国人民银行关于融资租赁登记系统的规定，国开行应在抵押时点（2015年12月）进行查询。
-- **国开行提交**：证据54页和58页，东源煤电公司、曲靖电力公司对案涉设备的权属证明材料及股东会决议，证明设备所有权属曲靖电力公司；招银租赁未对该组证据提出异议。
-- **国开行提交**：证据108页融资租赁登记信息核查表，证明其核查义务仅限于曲靖电力公司；招银租赁认为国开行应扩展调查东源煤电。
-- **招银租赁提交**：回租设备清单（证据第7页），载明设备名称、生产厂家、出厂日期2012年3月1日；国开行质证认为清单未载明设备型号，且其现场调查核实设备铭牌生产日期均在2013年以后，看不出是同一设备。
-- **招银租赁提交**：2013年和2015年审计报告（证据82页和95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行质证认为该报告已对设备出资事项进行载明，招银租赁应当知道设备出资情况。
-- **东源方提交**：2015年12月2日邮件及附件《东源公司融资情况统计表》，证明已告知国开行抵押设备与招银租赁设备名称一致；国开行质证认为该邮件系贷后审查材料，统计表中招银租赁栏记载抵押类型为不动产抵押，与本案融资租赁是两个法律概念，不能证明履行了告知义务。
+- **东源方提交**：2015年12月2日邮件及《东源公司融资情况统计表》，证明已向国开行告知招银租赁抵押物已登记、国开行抵押物正在办理，且两家公司抵押设备名称完全相同并用红色标注；国开行质证认为该邮件系贷后审查材料，不能证明已履行告知义务，且招银租赁栏记载的抵押类型为不动产抵押，与本案融资租赁是两个法律概念。
+- **国开行提交**：2018年9月对曲靖电力公司的融资租赁查询证书（证据第5组第1项），证明已尽查询义务；招银租赁质证认为该查询证书不符合要求，依据2014年93号中国人民银行规定，国开行应在抵押时点（2015年12月）进行查询。
+- **招银租赁提交**：回租设备清单（证据第7页），载明设备名称、生产厂家、出厂日期2012年3月1日；国开行质证认为清单未载明设备型号，且经现场调查核实，抵押设备铭牌生产日期均在2013年以后（部分2013年11月、12月，部分2014年3月），看不出是同一设备。
+- **招银租赁提交**：2013年和2015年审计报告（证据第82页、第95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行质证认为该两份审计报告已对设备出资事项进行载明，招银租赁有理由知道或应当知道设备出资情况。
+- **国开行提交**：证据第54页、第58页东源煤电公司、曲靖电力公司对案涉设备的权属证明材料及股东会决议，证明设备所有权属曲靖电力公司；招银租赁质证认为东源煤电的出资行为系无权处分，电力公司未取得设备所有权。
+- **国开行提交**：融资租赁登记信息核查表（证据第108页），证明已对曲靖电力公司名下融资租赁登记信息进行核查，未发现登记；招银租赁质证认为国开行应扩展调查东源煤电。
 ## 证人、鉴定与其他来源陈述
-- **东源方陈述**：东源公司以煤炭开采和经营为主营业务，受宏观经济下行影响，下游化工、钢铁、火电行业需求萎缩，2015年下半年出现资金链断裂，2019年2月19日法院受理破产重整时负债高达76.2亿元，去产能涉及安置职工13000多人，最困难时近半年未发工资，社会保险严重拖欠。
+- **东源方陈述**：东源公司系以煤炭开采和煤炭经营为主营业务的国有企业，受宏观经济下行影响，下游化工、钢铁、火电行业需求严重萎缩，2015年下半年出现资金链断裂，2019年2月19日人民法院受理破产重整时负债高达76.2亿元，去产能涉及安置职工13000多人，最困难时近半年未发工资，社会保险严重拖欠。
 ## 法官询问
-- **审判长询问**：生产设备作为动产，各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果？国开行答：系行业强制性规范，目的是防范动产可移动性和不明确性带来的金融风险；东源方答：系行业指导性规范，非强制性，不当然产生物权后果；招银租赁答：非法定物权登记，系权利公示，强化动产权利外观，可能产生对抗效力，但不影响所有权设立转移等法定效果。
-- **合议庭成员询问**：央行融资租赁登记系统有几种查询方式？能否保证查询到登记结果？国开行答：目前只能按查询单位一种方式查询；招银租赁答：可通过公司名称或设备情况两种方式查询，以设备查询涉及种类物区分问题。
-- **合议庭成员询问**：案涉5套设备登记时识别码是否登记清楚？招银租赁答：设备系种类物，无唯一识别码，当时未登记。
-- **合议庭成员询问**：国开行贷款前审查时，内部是否有规定必须查询融资租赁系统，未查到也要将未查到记录作为风控材料？国开行答：按央行规定需查询系统，因无记录未保留查询记录，内部无此规定。
-- **合议庭成员询问**：国开行认为查询了曲靖电力公司登记信息未查到结果，以此免责的逻辑？国开行答：作为金融机构按央行规定查询，抵押人是曲靖电力公司，查询后系统无融资租赁记录，至今也无记录，说明行为无过失。
-- **合议庭成员询问**：招银租赁在融资租赁登记系统是否登记设备唯一标识码？是否必填项？招银租赁答：不是必填项，案涉设备无唯一识别码，登记时无法填写。
-- **合议庭成员询问**：设备安装后发电机上是否有唯一标识码？招银租赁答：发电机铭牌上只有型号和参数，同型号设备铭牌相同。
-- **合议庭成员询问**：国开行和招银租赁认为违反查询规范多大程度才导致融资租赁司法解释第9条第2款法律后果？是基本查询义务还是全面审慎义务？国开行答：基本查询义务，针对抵押人曲靖电力公司已完成；招银租赁答：对银行业是严格义务，只要未查询就不构成善意，本案中设备信息足以引起注意。
-- **合议庭成员询问**：若银行通过其他途径知晓动产属融资租赁物，是否相当于已了解风控情况？国开行答：基本义务必须履行，通过其他渠道了解可能影响审批，但查询动作必须做；东源方答：金融机构接受抵押物前需确权并查询权利瑕疵，通过其他渠道知晓仍应查询；招银租赁答：仍须通过央行系统查询，因其他方式无法在争议中证明，只有确定标准才能衡量善意。
-- **合议庭成员询问**：各方对融资租赁司法解释第9条第2款举证责任分担如何理解？国开行答：按谁主张谁举证原则，争议焦点是查询范围和主体；招银租赁答：第1、2、4项由出租人举证，第3项由第三人（国开行）举证证明办理抵押时查询了央行系统。
-- **审判长询问**：双方如何看待不同登记机构产生的登记信息冲突？国开行答：动产抵押登记与融资租赁登记系统信息不统一导致矛盾，属系统性问题，建议整合信息；东源方答：系统整合或衔接有必要，但非专业机构提不出成熟建议；招银租赁答：可从立法层面统一要求、发挥行业协会作用、操作和技术层面实现信息互通，企业也应主动登记。
+- **审判长询问**：生产设备作为动产，各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果？国开行答：系行业强制性规范，目的是防范金融风险，防止动产多处抵押或融资租赁冲突；东源方答：系行业指导性规范，非强制性，不当然产生物权后果；招银租赁答：根据物权法定原则，非法定物权登记，只是权利公示，强化动产权利外观，可能产生对抗效力，但不影响所有权设立转移等法定效果。
+- **合议庭成员询问**：央行融资租赁登记系统有几种查询方式？能否保证查询到登记结果？国开行答：目前只能使用一种查询方式，即按查询单位查询；招银租赁答：可通过公司名称查询或设备情况查询，以设备查询涉及种类物区分问题。
+- **合议庭成员询问**：案涉5套设备登记时识别码是否登记清楚？招银租赁答：案涉5套设备系刚交付的种类物，无唯一识别码，当时未进行登记。
+- **合议庭成员询问**：国开行贷款前审查时，内部是否有规定必须查询融资租赁登记系统，未查到也要将未查到的单子作为风控材料？国开行答：按央行规定肯定要查询该系统，但因没有记录，未保留筛查记录，内部无此规定。
+- **合议庭成员询问**：国开行认为查询了曲靖电力公司登记信息但未查到结果，以此免责的逻辑？国开行答：作为金融机构按央行规定查询，因设备系通用设备无法查设备，只能查抵押人曲靖电力公司，查询后系统无记载，且至今也无记载，说明行为无过失。
+- **合议庭成员询问**：招银租赁在融资租赁登记系统是否登记设备唯一标识码？是否必填项？招银租赁答：不是必填项，案涉设备无唯一识别码，登记时无法填写；发电机铭牌只有型号和参数，上海电气出厂的15万伏发电机铭牌都一样。
+- **合议庭成员询问**：查询通知规定银行办理动产抵押前应到人民银行登记系统查询融资租赁情况，两方认为违反该规范多大程度才导致融资租赁司法解释第9条第2款法律后果？是基本查询义务还是全面审慎查询义务？国开行答：是基本查询义务，针对抵押人曲靖电力公司的审慎调查义务已完成；招银租赁答：是对银行业的严格要求，只要未查询就不构成善意，本案中综合信息能确定5台设备的唯一性和特殊性，已足够引起国开行注意。
+- **合议庭成员询问**：若银行通过其他途径了解到动产属融资租赁物，是否相当于已掌握风控情况无需查询？国开行答：基本义务必须做，查询动作完成即可得出结论；东源方答：金融机构接受抵押物前需确权并查询权利瑕疵，通过其他渠道知道可能存在租赁仍应查询；招银租赁答：仍须通过央行系统查询，因其他方式获知在争议解决时无法证明，只有确定标准才能衡量是否构成善意。
+- **合议庭成员询问**：各方对融资租赁司法解释第9条第2款举证责任分担如何理解？国开行答：按谁主张谁举证原则，争议焦点是查询范围和主体；招银租赁答：第1、2、4项由出租人举证，第3项由第三人（国开行）举证证明办理抵押时已查询，且国开行应扩展调查东源煤电。
+- **审判长询问**：我国无统一动产登记制度，双方如何看待不同登记机构产生的登记信息冲突？国开行答：系系统信息不完整、条块化分割问题，非哪个部门的问题，建议系统整合互联互通；东源方答：系统整合或衔接确有必要，但非专业机构提不出成熟建议；招银租赁答：可从立法层面统一要求、发挥行业协会作用、操作技术层面实现信息互通，企业也应主动做抵押或所有权登记。
 ## 争议焦点与辩论
-- **争议焦点一：国开行是否善意取得抵押权**
-  - **国开行主张**：抵押设备为通用设备，无唯一标识码，无法通过设备查询融资租赁登记；已按央行规定查询融资租赁系统，无曲靖电力公司登记记录，构成善意取得；审查义务仅限于抵押人曲靖电力公司，不能扩大到东源煤电。
-  - **东源方主张**：2015年12月2日邮件中融资情况统计表已用红色标注抵押设备名称与招银租赁一致，国开行作为专业金融机构应尽注意义务，进行适当核查避免重复抵押。
-  - **招银租赁主张**：国开行未在抵押时点（2015年12月）查询融资租赁系统，不构成善意；东源煤电系借款人且与抵押人曲靖电力公司构成100%全资控股关系，国开行审查义务应扩展至东源煤电；东源煤电出资行为系无权处分，电力公司未取得设备所有权。
-- **争议焦点二：罚息复息计算及起算日期**
-  - **国开行主张**：利息计算期间为2017年12月21日至2018年6月12日，利息合计21,795,727.68元；罚息自2018年6月13日起算至2019年2月19日，合计41,050,579.57元；复利自2018年3月21日起算至2019年2月19日，合计1,918,206.23元；2018年6月13日发函宣布贷款提前到期，罚息应自该日起算。
-  - **东源方主张**：合同约定宣布贷款提前到期应限期偿还，当天要求偿还8.37亿本金不合理，有违公平原则；罚息不能作为复利计算基数，有最高院2015年、2016年判例支持；复利再计算复利无合同依据。
-- **争议焦点三：东源煤电东源煤业是否应连带给付违约金**
-  - **国开行主张**：依借款合同第24条第3项，被上诉人违约应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续，举证责任在被上诉人。
-  - **东源方主张**：国开行未举证东源煤电违反柜台前移和账户管理约定，举证不能后果应自行承担；国开行未按合同约定发函限期纠正，无权主张违约金。
+- **争议焦点一：国开行是否尽到审查义务，是否构成善意取得抵押权**
+  - 国开行主张：审查义务仅限于抵押人曲靖电力公司，不能扩大到东源煤电；已按央行规定查询融资租赁登记系统，但未保留查询记录；案涉设备系通用设备，无唯一标识码，无法查设备；已对设备所有权尽审慎义务，构成善意取得。
+  - 东源方主张：2015年12月2日邮件已用红色标注两家公司抵押设备名称完全相同，国开行作为专业金融机构应尽注意义务进行核查区分；国开行未提供证据证明已做区分。
+  - 招银租赁主张：国开行应提供2015年12月抵押时点的查询记录而非2018年9月的查询证书；东源煤电系曲靖电力公司100%全资控股母公司，且系本案借款人，国开行对东源煤电的审查义务应当具备；东源煤电出资行为系无权处分，电力公司未取得设备所有权；招银租赁2012年已取得设备所有权，国开行2015年抵押在后且未审查，不构成善意。
+- **争议焦点二：一审判决对罚息复息的计算及起算日期是否认定错误**
+  - 国开行主张：利息计算期间为2017年12月21日至2018年6月12日，利息合计21,795,727.68元；罚息计算期间为2018年6月13日至2019年2月19日，罚息合计41,050,579.57元；复利计算期间为2018年3月21日至2019年2月19日，复利合计1,918,206.23元；2018年6月13日发函宣布贷款提前到期，罚息应自该日起算；合同第6条第4款明确约定对逾期借款利息按罚息利率计收复利，有合同依据。
+  - 东源方主张：合同第24条第2款第2项约定宣布贷款提前到期时应限期偿还，限期偿还与立刻偿还是不同概念，国开行当天发函要求立即偿还无合同依据，且未给合理期限有违公平；依据《人民币利率管理规定》第21条及最高院2015年、2016年判例，罚息不能作为复利计算基数；复利再计算复利无合同依据，应予以扣除。
+  - 招银租赁：不是借款合同当事人，尊重合议庭审查结果。
+- **争议焦点三：东源煤电、东源煤业是否应当连带给付违约金**
+  - 国开行主张：依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金；东源煤电未按合同第13条、第14条约定配合办理账户管理及柜台前移手续，举证责任在被上诉人；罚息复利违约金金额未超过法定最高标准。
+  - 东源方主张：国开行未举证证明东源煤电违反柜台前移和账户管理约定，举证不能后果应自行承担；按合同约定国开行应先限期纠正，未发纠正函无权主张违约金。
+  - 招银租赁：不是该合同参与方，尊重合议庭审查结果。
 # 庭审结果
-- **争议焦点一：国开行是否善意取得抵押权**：各方对融资租赁登记性质存在分歧，国开行主张系行业强制性规范，东源方主张系指导性规范，招银租赁主张非物权登记但具有对抗效力；合议庭未当庭认定。
-- **争议焦点二：罚息复息计算及起算日期**：国开行主张利息计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；东源方主张应给合理期限且罚息不应作为复利基数；合议庭未当庭认定。
-- **争议焦点三：东源煤电东源煤业是否应连带给付违约金**：国开行主张依合同约定支付千分之一违约金，东源方主张国开行未举证违约行为且未发函限期纠正；合议庭未当庭认定。
-- **调解结果**：各方当事人自愿达成调解协议，合议庭予以确认并出具调解书。
-  - 国开行对东源煤电的债权扣除破产清偿本金后，利息罚息复利合计6474.4513万元。
-  - 招银租赁对6项设备享有所有权，对应债权1377.4137万元；国开行对93项设备有抵押权。
-  - 案涉全部发电设备整体盘活处置，变现款双方各得50%，费用各担50%。
-  - 调解书生效后20日内由国开行向一审法院申请执行。
-  - 东源曲靖电力承担案涉设备管理费用并无条件配合司法处置。
-  - 各方对一审判决第2项、第4项无争议，按判项内容在调解书中确认。
-  - 一审诉讼费用中，国开行诉请部分按一审判决执行，招银租赁诉请部分由二审法院按规定计算后由国开行承担；二审诉讼费用由国开行和东源煤电各承担50%。
-  - 协议签订后，各方就本案涉及问题不再存在任何争议。</t>
+- **争议焦点一**：国开行是否尽到审查义务，是否构成善意取得抵押权。
+- **争议焦点二**：一审判决对罚息复息的计算及起算日期是否认定错误。
+- **争议焦点三**：东源煤电、东源煤业是否应当连带给付违约金。
+- **调解结果**：各方当事人自愿达成调解协议，合议庭予以确认，庭后出具调解书。
+- **债权债务确定**：国开行对东源煤电的债权扣除破产中已清偿的本金外，利息、罚息、复利合计6474.4513万元。
+- **设备权属确认**：在东源煤电、东源煤业破产重整程序中，已确定招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；确定国开行对93项设备有抵押权。
+- **设备处置安排**：招银租赁和国开行对案涉全部发电设备整体盘活处置，并从变现款中实现各自债权；调解书生效后20日内，由国开行向一审法院提出执行申请，启动司法处置程序，变现价款双方各得50%，实现费用双方各担50%。
+- **未实现债权处理**：国开行、招银租赁未实现的债权待执行法院出具体本裁定后，按照破产重整计划中的预留方案实现债权；若破产管理人对招银租赁的债权不予纳入预留方案，由东源煤电按照此前招银租赁在东源煤电破产重组程序中有担保清偿方案予以清偿。
+- **变现不能的后果**：若司法变现不能，国开行和招银租赁的权益通过前述方法实现后均放弃对案涉设备的权益，由东源曲靖电力自主生产经营。
+- **费用承担**：案涉设备上的管理费用由东源曲靖电力承担；东源曲靖电力无条件配合司法处置。
+- **无争议判项**：各方对一审判决第2项、第4项无争议，按照其判项内容在调解书中确认。
+- **诉讼费用**：一审诉讼费用中对于国开行诉请部分按照一审判决执行；对于招银租赁诉请部分的诉讼费用，由二审法院按照规定，根据争议财产对应的债权数额计算后，由国开行承担；二审诉讼费用由法院依法确定后，由国开行和东源煤电各承担50%。
+- **争议终结**：本协议签订后，各方之间就本案涉及的问题不再存在任何争议。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>84.7</v>
+        <v>91</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/4467</t>
+          <t>28485/4997</t>
         </is>
       </c>
     </row>
@@ -3224,47 +3229,45 @@
       <c r="C8" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持并汇报。验收组于18、19号提前介入项目摸排，20号召开首次会议，分内业、外业两方面对卢萨卡、蒙泽两点开展检查。卢萨卡点已完成除弹料加工调试以外的所有验收工作；蒙泽点已完成全部验收工作，并顺带完成带料调试和试生产；某皮卡点现场验收尚未开展，内业资料已提前拿到卢萨卡。内业资料基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需完善。外业检查中，建筑、安装、设备三部分总体质量良好，蒙泽点工艺设备运行正常，产能符合设计指标。财务方面符合规范。验收组提出人员履约、内业资料、现场实体等整改项，管理组和技术组回应将整改落实。合作局领导金昌柱要求分析蒙泽厂区混凝土路面开裂原因、出报告前完成整改并复核，公司领导林总强调交通安全和疫情防控。整体项目健康度良好，存在少量需整改问题。
+本次会议为原占比二玉米面加工厂项目中期验收会议，验收组于18、19号提前介入项目摸排，20号召开首次会议，分内业、外业两方面对卢萨卡、蒙泽两点开展检查。卢萨卡点已完成除弹料加工调试以外的所有验收工作，蒙泽点已完成全部验收并顺带完成带料调试和试生产；姆皮卡点现场验收尚未开展，内业资料已提前拿到卢萨卡。内业资料基本满足项目标准和规范要求，但竣工文件分类整理和签字规范性需完善；外业检查中建筑、安装、设备三部分总体质量良好，蒙泽点工艺设备运行正常，产能符合设计指标。财务账户设置、资金往来、银行开户等符合财务处理规范和标准。验收组提出人员履约、内业资料、现场整改等要求，管理组和技术组承诺会后细化并落实；合作局领导要求分析混凝土路面开裂原因、出报告前完成整改，公司领导强调按合同仔细验收并注意交通安全和疫情防控。
 # 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作，包括内业、外业检查 | ✅已完成 |
+| 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作，内业资料已提前拿到卢萨卡 | ✅已完成 |
 | 蒙泽点验收 | 已完成全部验收工作，并顺带完成带料调试和试生产，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
-| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡 | ⏸未开始 |
-| 内业资料检查 | 管理组和技术组按合同要求组建执行团队，编制施工组织计划、管理计划、实施细则和专项预案，内业资料基本满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需完善 | 🔄进行中 |
-| 外业检查-建筑部分 | 原材料使用符合合同要求，主材从国内采购或从卢萨卡集中采购，内在品质和外在表观达到良好标准 | ✅已完成 |
-| 外业检查-安装部分 | 钢结构材料从国内定制，施工工艺和外观质量满足规范和标准要求 | ✅已完成 |
-| 外业检查-设备部分 | 设备参照中国标准定制，厂家高峰期派十几名人员现场指导安装，蒙泽点工艺设备运行正常，产能符合设计指标，机电设备安装符合国家质量检验标准 | ✅已完成 |
-| 财务检查 | 账户设置、资金往来、银行开户等符合财务处理规范和标准 | ✅已完成 |
+| 姆皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡 | ⏸未开始 |
+| 内业检查 | 分管理组和技术组，按合同和规范开展，编制施工组织计划、管理计划、实施细则和专项预案，内业资料基本满足要求，但分类整理和签字规范性需完善 | 🔄进行中 |
+| 外业检查-建筑 | 原材料集中从国内采购或从卢萨卡大型供货单位采购，内在品质和外观质量良好，存在局部装饰装修损伤需修复 | 🔄进行中 |
+| 外业检查-安装 | 钢结构材料从国内定制，施工工艺和外观质量满足规范，监控管线接头脱落需全面检查 | 🔄进行中 |
+| 外业检查-设备 | 参照中国标准定制三套成套设备，厂家高峰期派十几名人员现场指导安装，蒙泽点工艺设备运行正常 | ✅已完成 |
+| 财务检查 | 财务账户设置、资金往来、银行开户等符合财务处理规范和标准 | ✅已完成 |
 # 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 蒙泽厂区混凝土路面开裂 | 中 | 少量开裂，可能影响项目移交后使用，存在大面积开裂隐患 | 王总（验收组） | 会同管理组、总包单位做专题技术研究，分析成因，制定科学合理整改方案，最迟出报告前完成整改，验收组复核 |
-| 卢萨卡点提升桶位置雨水倒灌 | 中 | 赞比亚雨季雨量大、风大，雨水可能倒灌 | 施工组 | 检查并考虑增加覆盖面积或采取技术措施解决 |
-| 廊桥横条分布稀疏 | 低 | 存在安全隐患，影响巡检维护人员安全 | 施工组 | 中间再加两个竖条，做一次检查和完善 |
-| 监控管线接头脱落 | 中 | 设备启动震动导致接头脱落，可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
-| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照等需完善，技术组人员统计未包含厂家服务人员，个别特种人员证件有效期问题 | 技术组 | 收集所有参与项目现场人员的护照证书，与国内人力资源对接，完善资料 |
-| 内业资料分类整理和签字规范性不足 | 低 | 竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需完善 | 技术组 | 按规范分类整理，汇总至卢萨卡并组卷 |
-| 某皮卡点路途遥远、交通状况不佳 | 中 | 存在交通安全风险，且正值雨季 | 验收组 | 注意交通安全和疫情防控，安全完成验收任务 |
-| 雨季厂区排水可能阻塞 | 低 | 屋面排水和室外通道可能阻塞 | 施工组 | 做一次最后的清理和排查工作 |
-| 成品保护有疏忽 | 低 | 工程实体完工时间较长，部分地方有破损 | 施工组 | 做好成品保护，及时修补破损 |
+| 混凝土路面开裂 | 中 | 某厂区非主要通道混凝土路面少量开裂，可能影响移交后形象，需分析原因并整改 | 管理组、总包单位 | 共同分析原因，制定科学合理的整改方案，出报告前完成整改，验收组复核 |
+| 设备管线接头脱落 | 中 | 监控管线接头脱落可能引起机械故障，需全面检查 | 技术组 | 伴随设备调试全面检查，保证有效性和安全性 |
+| 雨季排水隐患 | 中 | 雨季来临，屋面排水和室外通道可能阻塞，需清理排查 | 技术组 | 移交前检查厂区及办公区排水系统，清理阻塞 |
+| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照等需完善，技术组人员统计未包含厂家服务人员 | 管理组、技术组 | 收集所有参与项目现场人员的护照证书，完善人员统计 |
+| 内业资料分类整理不规范 | 中 | 竣工文件分类整理和签字规范性需完善，资料分散未集中 | 技术组 | 验收完成第一时间将三个厂区资料汇总于卢萨卡，分类组卷及编码 |
+| 不可预见费使用依据待完善 | 中 | 本项目有动用不可预见费的情况，依据证据和数据需充分无误 | 验收组、施工单位 | 后续专门对接，完善资料收集整理 |
+| 姆皮卡点路途交通安全 | 高 | 姆皮卡点路途遥远，路况不佳，存在交通安全风险 | 验收组 | 注意交通安全，做好疫情防控 |
+| 疫情风险 | 中 | 疫情形势特殊，影响人员履约和验收工作 | 验收组、参建单位 | 做好疫情防控，确保安全 |
 # 后续计划
-- **人员履约资料完善**：技术组龚总负责，已开展人员统计和护照收集，将收集所有参与项目现场人员的护照证书，完善进出场时间及证件有效期问题，确保验收报告闭合。
-- **内业资料汇总组卷**：技术组龚总负责，严格按照验收组要求及援外项目执行手册管理办法，在验收完成第一时间将三个厂区资料（含竣工图）汇总至卢萨卡，进行分类组卷及编码。
-- **现场实体整改**：技术组龚总负责，编制现场实体整改方案，对验收组提出的问题逐一整改落实，包括装饰装修损伤修复、厂区排水清理、混凝土路面开裂处理等。
-- **混凝土路面开裂专题研究**：验收组王总负责，会同管理组、总包单位等做专题技术研究，分析蒙泽厂区混凝土路面开裂成因，制定科学合理整改方案，最迟在出报告前完成整改，验收组复核。
-- **设备管线检查**：施工组负责，全面检查监控管线接头脱落问题，保证有效性和安全性，防止引起机械故障。
-- **屋顶廊桥完善**：施工组负责，检查卢萨卡点提升桶位置雨水倒灌问题，必要时增加覆盖面积或采取技术措施；加密廊桥横条，保障巡检维护人员安全。
-- **不可预见费资料完善**：验收组负责，与施工单位对接，完善动用不可预见费的依据、证据和数据，确保充分无误。
-- **某皮卡点现场验收**：验收组负责，会后及时安排，注意路途交通安全和疫情防控。</t>
+- **人员履约整改**：管理组和技术组会后细化验收组提出的问题，技术组正在收集所有参与项目现场人员的护照证书，完善人员统计（含厂家服务人员）及个别人员进出场时间、护照等资料，确保验收报告闭合。
+- **内业资料汇总**：技术组承诺在验收完成第一时间将三个厂区资料（含竣工图）汇总于卢萨卡，按援外项目执行手册管理办法进行分类组卷及编码，验收组可配合补充完善。
+- **现场实体整改**：技术组编制整改方案，对装饰装修损伤、卫生、排水、混凝土路面开裂、监控管线接头脱落、廊桥加固等问题逐一整改落实。
+- **路面开裂专项分析**：管理组和总包单位共同分析混凝土路面开裂原因（结合赞比亚气候特点），制定科学合理的整改方案，最迟在出报告前完成整改，验收组进行复核。
+- **成品保护与修补**：在移交外方前继续做好成品保护，对破损部位及时修补，雨季前检查厂区及办公区排水系统。
+- **姆皮卡点验收**：验收组会后安排前往姆皮卡点开展现场验收，注意交通安全和疫情防控，内业资料已提前拿到卢萨卡。
+- **不可预见费资料完善**：验收组与施工单位对接，完善不可预见费使用的依据证据和数据，确保充分无误，后续专门沟通。</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>62.7</v>
+        <v>58.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/2298</t>
+          <t>11110/2106</t>
         </is>
       </c>
     </row>
@@ -3475,89 +3478,90 @@
       <c r="C9" t="inlineStr">
         <is>
           <t># 发布会概况
-本次中金宏观策略周会由中金公司策略组主办，策略组刘刚凯文主持，于周一上午面向投资者召开，围绕大美丽法案、关税政策、港股流动性、光伏反内卷、人形机器人及游戏板块等热点展开分析。会议分四块内容：宏观策略部分解读大美丽法案对美股、美债、美元及港股流动性的影响，并更新关税谈判进展；行业层面邀请公用事业风光首席分析师刘佳妮分析光伏反内卷，机械军工分析师郭文秀分享人形机器人三季度趋势，传媒行业首席分析师张雪琴更新游戏板块投资机会。整体基调为结构性行情下在合适位置布局长期正确板块，美股美债波动提供再配置机会，光伏行业底部企稳，人形机器人关注三条主线，游戏板块调整后有望戴维斯双击。关键数字锚点包括：纳斯达克从底部反弹35%、大美丽法案提高债务上限约5万亿美元、6月游戏版号单月发放158个创2018年以来新高。会议未设问答环节，主持人提示投资者可直接联系对应分析师获取细节。
+中金公司策略组于周一上午举办宏观策略周会，由策略组刘刚凯文主持，面向投资者汇报大美丽法案、关税更新及港股流动性三大宏观议题，并邀请公用事业风光首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别分享光伏反内卷、人形机器人、游戏板块观点。会议整体基调为：大美丽法案短期带来流动性压力但中长期有利于信用周期，关税影响可控且市场逐渐脱敏，港股流动性边际收紧但非主导变量，建议在合适位置布局长期正确板块。关键数字锚点包括：大美丽法案提高债务上限约5万亿美元、每年额外支出约3400亿美元；关税有效税率当前约10-12%；6月游戏版号单月发放158个（2018年以来最高）。会议未设问答环节，主持人提示投资者可直接联系对应分析师获取进一步信息。
 # 核心信息
-## 大美丽法案与宏观策略
-- **法案三大内容**：`大美丽法案`包含三项核心内容——①提高债务上限约**5万亿美元**，消除违约风险并恢复政府融资能力；②延长`2017年减税法案`（非新增减税），每年额外支出约**3400亿美元**、总计**3.4万亿美元**，同时削减其他支出（含减少新能源补贴约**1.4万亿美元**）；③取消`899条款`（对海外投资者持有美债利息所得征税），避免主权基金抛售美债、维护美元体系根基。
-- **财政与赤字测算**：关税收入每年约**3000–4000亿美元**，可覆盖每年3400亿美元额外支出，财政赤字率基本维持在**5–6%**，不会大幅扩张；关税必须执行以支撑收入，否则赤字压力将引发市场担忧。
-- **三季度流动性影响**：7–9月财政部需发债并回补`TGA账户`，带来约**1万亿美元**额外供给（参照`2023年三季度`发债1万亿美元推高美债利率从3.8%至5%、美元走强、美股小幅下跌4–5%）；本次美债利率上行幅度或不及2023年，因`期限溢价`已处于**2013年以来高点**，但需关注需求端能否对冲。
-- **美股美债判断**：信用周期三个因素（政府、AI产业投资、私人部门需求）中财政因素环比改善，判断**四季度美元可能小幅走强、美股可能反弹跑赢**；三季度存在流动性波折（大美丽法案、关税、7月FOMC会议、7–8月通胀边际走高、中报业绩期），波动提供再配置机会，整体不悲观。
-## 关税政策更新
-- **四点核心判断**：①关税一定会做，用于支撑财政收入；②需维持一定税率（当前豁免10%水平）以收上来3000–4000亿美元；③不能太高，否则通胀受不了；④市场逐渐脱敏，静观其变。
-- **税率变化与有效税率**：新变化为时间拖后（原定7月9日达成）、大部分国家税率相比`4月2日对等关税`水平回落（除巴西外）；加拿大、墨西哥、欧盟因贸易占比高需单独谈判稳住，其他国家即便增加一倍也不影响有效税率（最高日本占比仅4.5%）；测算有效税率当前约**10–12%**，8月1日若全回去或提高则回到**10–15%**，最极端**18%**。
-- **通胀与美联储路径**：有效税率未大幅提高，通胀压力可控但会缓慢抬升，年底升至**3.3–3.4%**左右；即便18%水平也不大幅改变通胀路径；美联储7月降息勉强，9月及四季度之后仍可降息。
-- **对华关税与转口限制**：对华关税约**40–50%**（2018年约20%为基数）；`越南协议`和`英国协议`均含转口限制，越南转口限制为**40%**，低于对华税率，需密切关注；除8月1日与其他市场谈判外，需关注**8月12日中美谈判**进展及转口限制。
+## 大美丽法案
+- **法案三大内容**：提高债务上限约5万亿美元，消除违约风险；延长2017年减税法案（每年额外支出约3400亿美元，总计3.4万亿美元，同时削减含新能源补贴在内的其他支出约1.4万亿美元）；取消`899条款`（对海外投资者持有美债利息所得征税），消除主权基金及海外投资者不持有美债的障碍。
+- **财政与赤字测算**：当前约10%的关税税率每年带来关税收入3000–4000亿美元，可覆盖每年3400亿美元额外支出，测算赤字率基本维持在5–6%，不会大幅增加；关税必须实施以支撑收入，否则赤字压力上升。
+- **流动性影响**：7–9月财政部需发债约1万亿美元（参照2023年三季度发债1万亿美元推高美债利率从3.8%至5%、美元走强、美股小幅下跌4–5%），本次供给确定但幅度或不及2023年——期限溢价已处2013年以来高点，美债利率抬升到5%以上可能性较低；美元流动性三季度边际收紧，但需求端可部分对冲。
+- **中长期判断**：基于信用周期框架（政府、AI产业投资、私人部门需求三部分），美国下半年环比改善、中国面临高基数，四季度美元可能小幅走强、美股可能反弹跑赢；美股美债波动提供再配置机会，整体不悲观。
+## 关税更新
+- **四点核心判断**：关税大概率实施（用于支撑收入）；需维持当前约10%的豁免税率以收上来3000–4000亿美元；税率不能过高（过高通胀受不了）；市场逐渐脱敏，静观其变。
+- **有效税率测算**：当前有效税率约10–12%（豁免水平），若8月1日关税全回去并提高，回到10–15%，最极端情况回到18%；相比4月2日对等关税水平大部分国家税率回落，除巴西可能大幅增加；加拿大、墨西哥、欧盟因贸易占比高需单独谈判稳住，其他国家即便增加一倍也不影响有效税率（最高日本占比仅4.5%）。
+- **时间与通胀**：谈判时间变相延后（原定7月9日未达成）；通胀压力缓慢抬升，年底约3.3–3.4%，即便18%有效税率也不大幅改变通胀路径；美联储7月降息勉强，9月及四季度后仍可降息。
+- **对华关税与转口限制**：对华关税约40–50%（2018年约20%基础上）；越南、英国达成的协议均含转口限制（越南转口限制40%），需关注8月1日与其他市场谈判及8月12日中美谈判进展，尤其转口限制。
 ## 港股流动性
-- **三季度流动性偏紧**：美元流动性供给压力（7–9月美债供给增加）叠加港币未完全回到强方（港币汇率在**7.84–7.85**），金管局投放大量资金导致`HIBOR`利率大幅下降、微观流动性释放，但为维护`联系汇率制度`（7.75–7.85区间）金管局必然回收流动性，可小幅收（如收90亿、放1000多亿）以延缓收紧速度；三季度流动性供给不如二季度，IPO融资较多也形成约束。
-- **市场点位与风格建议**：指数在**23000–24000点**区间震荡，上不去也下不来；建议低迷时积极介入、亢奋时适度锁定利润；长期方向为两头——分红端（银行股溢价已低于**20%**，除保险外港股买银行股息率扣税后优势不大，短期透支但长期相对国债利率仍有空间，**125%**为隐形底）与成长端（新消费较拥挤、创新药稍降，科技硬件与AI应用相比3月已大幅降温，提供提前埋伏机会）；中期关注创新药、人形机器人、AI应用、短视频生成、软件等方向催化剂。
-## 光伏行业反内卷
-- **行业供需失衡背景**：全球新增光伏装机从2020年**130GW**增至2024年**530GW**（CAGR **42%**），2025–2026年需求增速预计回落至**10%**左右；2025年全球需求预计**650–700GW**，但供给侧产能严重过剩——电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来产业链价格下跌**70–90%**，硅片电池自`2023年四季度`亏损、硅料组件自`2024年二季度`亏损，目前未见企业退出。
-- **反内卷政策升级**：2024年以行业协会主导为主（`2024年5月17日`光伏行业协会在工信部电子信息司指导下召开`光伏行业高质量发展座谈会`，提出产能建设指导、保护新技术、打击低于成本销售、鼓励兼并重组；10月、12月继续召开座谈会但收效不明显）；2025年政策级别提升——`2月国常会`提出化解重点产业结构性矛盾，`6月29日`起连续5天高层三次发声（`人民日报`发文指出光伏高投入低产出、阶段性供需错配、政绩观错位等问题），`7月1日`总书记主持`中财委第6次会议`提出依法依规治理低价无序竞争、推动落后产能退出，`7月3日`工信部召开光伏企业座谈会强调技术创新与产能升级；具体干预措施尚未披露。
-- **各环节整合难度**：硅料最易切入——集中度高（在产企业不到20家）、成本曲线最陡峭（丰水期边际现金成本约**38元/公斤**，颗粒硅约**28元/公斤**，尾部厂商高达**45元/公斤**）、供需比超**200%**、作为最上游影响全产业链定价，整合最迫切；电池片供需最好——`PERC`电池约500GW已基本退出、`TOPCon`占**90%**市场份额、`BC`技术单月渗透率提升至**5–6%**；组件环节分散（企业几十上百家）整合较难；光伏玻璃自`2024年9月`第一波产能出清（有效产能降幅约**6%**）后，协会呼吁降产保价、7月起第二轮出清计划降产**30%**，测算需出清约**2万吨**方可修复供需平衡，当前价格已创历史新低、龙头企业经营性成本约**1元/平方米**。
-- **市场反馈与价格信号**：官媒发声、中财委会议及工信部座谈会后，多晶硅期货价格大幅反弹、上周五触及**40元/公斤**；现货报价较前一周（约35元）大幅上涨，前期已签订单执行力度增强，硅料市场呈现触底企稳态势；硅片报价上涨约**10%**、电池上涨约**2分钱**，过去两周硅料和玻璃股价上涨**20–30%**；组件价格有跟涨意愿，但下游电站受`136号文`（新能源全面入市）影响电价不确定性增加，能否接受涨价传导需观望招标情况，组件环节涨幅相对靠后约**10%**。
-- **穿越周期能力**：头部一体化组件企业可通过收现款再发货、占用上游供应商账期获得正向经营现金流，财务压力小于上游；关注低杠杆、强现金、强融资能力企业（部分资产负债率仅**10%出头**）；技术变革持续——颗粒硅使用比例从10–20%提升至**50%**、硅片薄片化与细线化、钨丝全面导入、浆料铜替代银将于2025–2026年大规模导入、`TOPCon`逐步取代`PERC`。
+- **流动性边际收紧**：7–9月美元流动性供给压力叠加港币汇率7.84–7.85（金管局需回收流动性，可小幅收如收90亿、放1000多亿以延缓收紧速度），三季度流动性供给不如二季度；IPO融资较多也形成约束；港股指数在23000–24000区间震荡。
+- **风格与配置建议**：长期方向仍是两头——分红端银行股溢价已低于20%（除保险外港股买银行股息率扣税后优势不大，短期透支，但相对国债利率仍有空间，短期1.25%是隐形底）；成长端新消费较拥挤、创新药稍降，科技硬件、AI应用拥挤度相比3月份大幅下降，提供提前埋伏机会。
+- **中期方向**：创新药、人形机器人、AI应用、短视频生成、软件等可能逐渐有催化剂；总原则是在合适位置拿长期正确的板块，低迷时积极介入、亢奋时适度锁定利润。
+## 光伏反内卷
+- **行业供需失衡**：全球新增光伏装机从2020年130GW增至2024年530GW（4年CAGR 42%），2025–26年增速预计回落至10%上下（基数变大、电网平衡制约）；2025年全球需求预计650–700GW，供给侧电池产能是需求1.5倍、硅片组件2倍、硅料2.5倍；2022年以来产业链价格下跌70%–90%，硅片电池自2023年四季度亏损、硅料组件自2024年二季度亏损，尚未见企业退出。
+- **反内卷政策升级**：2024年5月17日光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会（强调市场化手段、政府有形手作用，提出产能建设指导管理、保护新技术、打击低于成本销售、鼓励兼并重组），2024年10月、12月企业减产自律但收效不明显；2025年2月国常会提出化解重点产业结构性矛盾，6月29日人民日报发文《在破除内卷式竞争中实现高质量发展》（指出光伏高投入低产出、阶段性供需错配、高标准市场体系尚待健全、部分地方政绩观错位），7月1日总书记主持中财委第六次会议提出依法依规治理企业低价无序竞争、引导产品品质、推动落后产能退出，7月3日工信部召开光伏企业座谈会（指出技术创新、产业产能升级是反内卷重要手段）；目前未见具体干预措施披露。
+- **硅料环节整合最迫切**：在产企业不到20家、集中度最高；成本曲线最陡峭（丰水期边际现金成本约38元/公斤，颗粒硅约28元/公斤，尾部厂商高达45元/公斤）；供需比超200%（高于硅片电池组件150%左右）；作为最上游影响全产业链定价；下游电池组件分散（组件企业几十上百家），整合较难。
+- **价格与产能出清**：多晶硅期货价格上周五触及40元/公斤（前一周现货约35元，上周报价大幅上涨），硅片报价涨约10%、电池涨约2分钱，组件涨幅相对靠后约10%；光伏玻璃2024年9月第一波产能出清（有效产能降幅约6%），协会呼吁降产保价、7月开始第二轮出清（参加企业计划降产30%），测算需出清约2万吨方可修复供需平衡，当前价格创历史新低、龙头企业经营性成本约1元/平方米，不排除亏损幅度加大；组件价格跟涨需观望下游电站受`136号文`（新能源全面入市）影响下的招标情况。
+- **穿越周期能力**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流，财务压力小于上游；关注低杠杆、强现金、强融资能力企业（部分资产负债率仅10%出头）；技术变革持续——颗粒硅使用比例从10–20%提升至50%、硅片薄片化、钨丝全面导入、浆料铜替代银2025–26年大规模导入、Topcon电池取代PERC（PERC基本退出市场、Topcon占90%份额、BC渗透率单月提升至5–6%）。
 ## 人形机器人
-- **二季度回顾与回调原因**：二季度A股机器人板块按流通市值加权平均下跌约**9%**，跑输机械设备板块约**12个百分点**；特斯拉核心供应商标签股从3月高点普遍回调**30–40%**，5–6月交易型资金止损明显；回调主因是特斯拉4月宣布量产时间线延后、叠加中美关税降低风险偏好，但产业端国内软硬件技术突破与资本运作催化密集。
-- **主线一：华为云生态开放**：`6月底`华为开发者大会首发`盘古世界模型`，通过时空可控生成技术实现2D视频模态与3D激光点云模态像素级对应，为首个支持点云和视频双模态同时生成的大模型；`CloudRobot`平台构建三大能力——多模态生成模型（泛化训练环境）、规划大模型（复杂物理世界自主决策）、执行大模型（操作精度提升至**毫米级**）；华为明确不造机器人，以`RTC`方式向全社会开放，有望探索`AI agent`收费或`license`收费模式；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作。
-- **主线二：本土企业技术闭环**：`智元机器人`拟通过收购材料厂商在A股上市，具备AI+双足及轮式人形机器人全栈能力，相关汽车零件、消费电子零部件、机械零部件厂商股价出现底部异动；`宇树科技`年收入突破**10亿元**，下半年有望加速上市；智元与宇树同时中标中国移动旗下接近**1.2亿元**人形机器人采购订单，将部署于移动营业厅与消费者互动；建议优先关注投资回报率明确的场景（物流端降低单件运输成本为2025年下游刚需）；国内人形机器人本体厂商至少**100家以上**。
-- **主线三：特斯拉延期与硬件替代**：`Optimus`存在电机过热、灵巧手负载不足、续航问题，特斯拉正在变更方案并筛选供应商；这些硬件瓶颈为行业共性瓶颈——电机过热方面已有上市公司发布新款无框力矩电机（改善散热性能），续航方面轻量化（以塑代钢、替代铝合金）成为方向。
-- **市场与投资信号**：二季度港股机器人板块估值溢价明显（PE、PS均显著），源于稀缺性与流动性红利（进入港股通或相关指数后享受全球科技资金关注）；下半年港股机器人板块有确定性扩容，关注A+H动向；三季度建议关注三类信号——华为云生态接入厂商新增趋势、头部企业出货量跨越**年化500台或1000台**、电机硬件优化窗口；技术创新、产业需求、工厂替代三重周期共振时孕育投资机会。
+- **二季度回顾**：A股机器人板块4–6月按流通市值加权平均下跌约9%，跑输机械设备约12个百分点；特斯拉核心供应商标签股从3月高点普遍回调30%–40%；5–6月交易型资金止损明显；回调主因是特斯拉4月后宣布量产时间线延后叠加中美关税降低风险偏好，标签股难创新高、资金涌向小盘微盘扩散行情。
+- **华为云生态主线**：6月底华为开发者大会首发`盘古世界模型`（时空可控生成技术，首个支持点云和视频双模态同时生成的大模型，解决训练物理模型痛点）；`CloudRobot`平台构建三大能力——多模态生成模型（泛化训练环境）、规划大模型（复杂物理世界自主决策）、执行大模型（操作精度提升至毫米级）；华为明确不造机器人，以RTC方式向社会开放，有望探索AI agent收费或license收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作，云智能+场景深耕模式下半年有望更多落地。
+- **本土企业技术闭环主线**：智元机器人拟通过收购材料厂商在A股上市（具备AI+双足及轮式人形机器人全栈能力），相关零部件厂商股价底部异动；宇树科技年收入突破10亿元、下半年有望加速上市；智元、宇树同时中标中国移动旗下接近1.2亿元人形机器人采购订单（部署移动营业厅与消费者互动）；国内人形机器人本体厂商至少100家以上，优先关注投资回报率明确的场景（物流端降低单件运输成本是2025年下游明确刚需）。
+- **特斯拉硬件替代主线**：Optimus存在电机过热、灵巧手负载不足、续航问题，整体变更方案、供应商仍在筛选；电机过热对应无框力矩电机新品（改善散热性能）、续航对应轻量化方向（以塑代钢、替代铝合金）；特斯拉暴露的硬件瓶颈是行业共性瓶颈，提供硬件替代窗口期。
+- **投资信号与展望**：三季度是二季度迷茫期到商业兑现的过渡阶段，关注三类信号——华为云生态接入厂商三季度继续新增、头部企业出货量跨越年化500台或1000台（背后股价及供应商演绎机会）、聚焦电机硬件优化窗口；港股机器人板块二季度估值溢价明显（PE、PS均高），源于稀缺性和流动性红利（进入港股通或相关指数后享受全球科技资金关注），下半年有确定性扩容，关注A+H动向。
 ## 游戏板块
-- **政策支持与版号发放**：`2025年1月、3月`国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门政策支持包（含中小微企业奖励、数字内容文化产业出海支持、IP方向）；`6月`版号单月发放**158个**（国产**147个**、进口**11个**），为**2018年以来单月最高**，每月同时发放国产与进口版号，版号不再是产品上线障碍。
-- **市场规模与新品周期**：`2024年8月`以来游戏市场单月持续正增长；`2025年1–5月`游戏市场规模同比增长**17%**（规模1400多亿元），手游同比增长**20%**；今年缺乏大厂大作（腾讯、网易重点产品多落在明年，米哈游无重磅作品），但中型厂商新品成为核心催化——吉比特`《仗剑传说》`（5–6月上线）首月流水**2亿多元**，巨人网络`《超自然行动组》`6月预估流水**过亿**（乐观年化约**20亿元**流水量级，利润提升达**50%以上**）；大厂缺大体量产品时中型厂商获客友好，国内大多数新游用户ROI表现良好。
-- **估值与投资判断**：当前游戏板块TTM PE约**30倍**、2025年静态PE约**20倍**（切明年更低），低于`2023年`AI行情时的**45倍**；游戏板块与两年前不同——具悦己型消费属性、逆周期性（1–5月同比增长17%、新品不受限）、政策环境完全转变；新品利润有滞后性（买量成本投入与流水递延确认差异），今年上新品的利润更多在**明年兑现**；建议跟踪新品市场表现、用户获取下载榜排名等领先指标；在消费、政策、新品周期三重利好下，游戏板块调整后有望再次实现**戴维斯双击**，当前是配置时间点。
+- **政策环境**：去年`黑神话悟空`爆火后游戏行业文化价值和经济价值获广泛认可，政策支持力度空前；今年1月、3月国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门政策支持包（含中小微企业奖励、数字内容文化产业出海支持、IP方向）；政策帮助企业稳定军心、长周期运营，短期修复多年压制的估值。
+- **版号发放**：去年四季度以来版号每月正常发放，今年已进化到每月同时发国产和进口网络游戏版号；6月单月发放158个（国产147个、进口11个），为2018年以来单月最高水平；版号不再是产品研发到上线的障碍，而是正常审批流程，助力暑期档新品推出。
+- **市场规模**：2024年8月以来游戏市场单月持续正增长（版号停发时增速曾掉到0以下）；2025年1–5月游戏市场规模同比增长17%（1400多亿元），手游同比增长20%。
+- **新品周期**：今年市场原预期缺乏产品大作（腾讯、网易上半年和下半年重点产品相对较小，未上市的米哈游也无重磅作品），但中型厂商新品成为A股、港股中型公司核心催化——吉比特5–6月上线的`仗剑传说`首月流水2亿多元、巨人网络`超自然行动组`6月流水过亿（年化乐观约20亿元，利润提升50%以上）；大厂缺少大体量产品时中型厂商获客友好（对比去年员工和蛋仔竞争推高流量价格），国内大多数新游用户ROI表现良好。
+- **估值与展望**：当前TTM PE约30倍、2025年静态PE约20倍（2023年AI行情下到过45倍）；游戏板块与两年前不同——属悦己型消费领域、受宏观经济影响小（1–5月同比增长17%）、政策环境完全改变、新品周期延续（7月中三七上线斗罗，网易腾讯等新品更多落在明年大周期）；新品利润有滞后性（买量成本投入与流水递延确认差异），今年上新品的利润明年兑现；建议关注新品市场表现、用户获取下载榜排名等领先指标，短期估值提升仍有空间，在消费、政策、新品周期三重利好下调整后有望实现戴维斯双击。
 # 官方表态
-## 宏观策略｜大美丽法案与美元流动性
-- **去美元化共识过度拥挤**：市场把美元弱等同于去美元化、把美元弱与美股弱直接划等号，均属误区；美元弱在多数时候（非抛售美国资产情形）对美股有利，因海外收入占比高、可形成金融条件宽松。
-- **信用周期框架判断**：美国经济如篝火，不泼冷水即自然修复；中国经济如煮水，需持续添柴。下半年美国形成低基数、可能环比改善，中国面临高基数，边际上或此消彼长。
-- **大美丽法案三大内容**：提高债务上限约5万亿美元，消除违约风险；延长2017年减税法案（非新增减税），每年额外支出约3400亿美元、总计3.4万亿美元，同时削减新能源补贴等支出1.4万亿美元；取消899条款，避免海外投资者因税负抛售美债。
-- **财政赤字可控**：当前约10%以上关税税率每年带来关税收入3000–4000亿美元，可覆盖每年3400亿美元额外支出，财政赤字率基本维持在5–6%，不会大幅增加。
-- **三季度流动性抽水**：7–9月财政部需发债约1万亿美元并回补TGA账户，带来额外供给；参照2023年三季度（发债1万亿推高美债利率从3.8%至5%、美股小幅下跌4–5%），本次期限溢价已处2013年以来高位，利率抬升幅度或不及2023年，但需过流动性这道坎。
-- **美股美债观点**：对美股不悲观，4月中旬底部不能再做空；但当前涨幅已兑现较多预期，性价比不高，波动出现后提供再配置机会。
-## 宏观策略｜关税政策
-- **四点核心判断**：关税一定要做（支撑财政收入）；需维持一定税率（当前豁免10%水平即可收上3000–4000亿美元）；不能太高（通胀受不了）；市场逐渐脱敏、静观其变，高威胁税率可能是谈判技巧。
-- **新变化**：达成时间由7月9日变相拖后；除巴西外大部分国家税率相比4月2日对等关税水平回落；加拿大、墨西哥、欧盟因贸易占比高需单独谈判稳住，其他国家即便税率翻倍对有效税率影响很小（最高日本占比仅4.5%）。
-- **有效税率测算**：当前约10–12%，若8月1日关税全回去甚至提高，回到10–15%，最极端18%；对通胀影响可控，年底通胀或缓慢升至3.3–3.4%，不大幅改变路径；美联储7月降息勉强，9月后仍可降。
-- **对华关税关注点**：对华关税约40–50%（2018年约20%基础上）；越南、英国协议均含转口限制（越南转口限制40%），需关注8月12日中美谈判进展及转口限制条款。
-## 宏观策略｜港股流动性
-- **三季度流动性边际收紧**：美元流动性供给压力、港币尚未完全回到7.75强方（近期在7.84–7.85）、IPO融资较多，均形成约束；金管局可小幅收紧（如收90亿、放1000多亿）延缓利率上升速度，但联系汇率制度下一定会收。
-- **美元美债非港股唯一变量**：自身基本面强可盖过外部影响，单变量看略偏负面；港股内部极致分化，结构性行情集中在AI互联网、创新药、新消费及后续可能重回焦点的人形机器人、AI应用、游戏、软件等方向。
-- **点位与风格建议**：指数在23000–24000区间上不去也下不来，类似3月底震荡；低迷时积极介入、亢奋时适度锁定利润；长期方向仍是两头分红，但银行股溢价已低于20%，短期有所透支，1.25%股息率仍是隐形底；成长端新消费较拥挤、创新药稍降，科技硬件与AI应用拥挤度较3月大幅下降，可提前布局。
-## 光伏｜反内卷
-- **政策升级**：2025年6月29日起连续发声——人民日报发文指出光伏高投入低产出、阶段性供需错配、高标准市场体系尚待健全、部分地方政绩观错位等问题；7月1日中财委第6次会议提出依法依规治理企业低价无序竞争、引导产品品质、推动落后产能退出；7月3日工信部召开光伏企业座谈会，指出技术创新与产业产能升级是反内卷重要手段；具体干预措施尚未披露。
-- **行业整合判断**：硅料环节最易切入整合——集中度高（在产企业不到20家）、成本曲线最陡峭（颗粒硅现金成本约28元/公斤、尾部厂商高达45元/公斤）、供需比超200%且为产业链最上游影响定价；电池片环节供需最好（Perc电池基本退出、Topcon占90%份额、BC渗透率单月达5–6%）；组件环节分散（几十上百家企业）整合最难。
-- **光伏玻璃自律出清**：2024年9月第一轮产能出清有效产能降幅约6%；当前协会呼吁降产保价，参加企业计划7月起降产30%，需出清约2万吨方可修复供需平衡；价格已创历史新低，龙头企业经营性成本约1元/平方米，后续不排除亏损加大推动出清。
-- **市场反馈**：多晶硅期货价格大幅反弹、上周五触及40元/公斤，现货报价较前一周35元左右大幅上涨，硅片报价涨约10%、电池涨约2分钱，硅料和玻璃板块股价过去两周上涨20–30%；组件环节涨幅相对靠后（约10%），下游电站受136号文新能源全面入市影响、电价不确定性增加，能否接受涨价传导需观望招标情况。
-- **穿越周期企业特征**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流；低杠杆、强现金、强融资能力企业财务健康度显著优于同行；持续技术创新（颗粒硅使用比例从10–20%提升至50%、硅片薄片化、钨丝导入、铜替代银2025–26年大规模导入）可帮助企业逆势获得份额。
-## 人形机器人｜三季度三条主线
-- **华为云生态开放**：6月底华为开发者大会首发盘古世界模型，为首个支持点云和视频双模态同时生成的大模型，解决训练物理模型痛点；CloudRobot平台构建多模态生成、规划、执行三大模型能力（操作精度提升至毫米级）；华为明确不造机器人，以RTC方式开放，有望探索AI agent或license收费模式；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作。
-- **本土企业技术闭环**：智元机器人拟通过收购材料厂商在A股上市，具备AI+双足及轮式人形机器人全栈能力；宇树科技年收入突破10亿元、下半年有望加速上市；智元与宇树同时中标中国移动旗下接近1.2亿元人形机器人采购订单，将部署于移动营业厅与消费者互动；物流端降低单件运输成本是2025年下游明确刚需，国内本体厂商超100家。
-- **特斯拉延期带来硬件替代窗口**：Optimus存在电机过热、灵巧手负载不足、续航问题，特斯拉正在变更方案并筛选供应商；电机散热（无框力矩电机新品）、轻量化（以塑代钢、替代铝合金）是共性瓶颈突破方向；港股机器人板块二季度估值溢价明显（PE、PS均高），下半年有确定性扩容，可关注A+H动向。
-- **三季度关注三类信号**：华为云生态接入厂商继续新增；头部企业出货量跨越年化500台或1000台；聚焦电机硬件优化对应的窗口期。
-## 游戏｜政策与产品周期
-- **政策支持力度空前**：今年1月和3月国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门政策支持包（含中小微企业奖励、出海支持、IP方向）；版号发放常态化，6月单月发放158个（国产147个、进口11个），为2018年以来单月最高水平。
-- **行业景气度**：2025年1–5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%；自2024年8月以来单月持续正增长；游戏在当前消费趋势下属悦己型消费领域，逆周期性明显。
-- **新品周期判断**：今年缺乏大厂大作（腾讯、网易重点产品相对少，米哈游亦无重磅作品），但中型厂商新品成为核心催化——吉比特《仗剑传说》首月流水2亿多、巨人网络《超自然行动组》6月流水过亿（年化乐观约20亿元、利润提升50%以上）；大厂缺少大体量产品时中型厂商获客友好，国内多数新游获客ROI良好。
-- **估值与展望**：当前TTM PE约30倍、2025年静态PE约20倍，低于2023年AI行情时的45倍；新品利润有滞后性、明年兑现，表观估值不便宜但明年业绩确定性提供支撑；建议跟踪新品市场表现、用户获取下载榜排名等领先指标；在消费、政策和新品周期三重利好下，游戏板块有望在调整后再次实现戴维斯双击。
+## 大美丽法案
+- **债务上限**：提高约5万亿美元，消除违约风险，使政府可继续发债支出；若假设GDP不增长，债务占GDP比例或达135%。
+- **减税延续**：非新增减税，主要为延长2017年减税法案，避免年底自动大幅加税；每年额外支出约3400亿美元、总计3.4万亿美元，同时削减新能源补贴等支出约1.4万亿美元。
+- **取消899条款**：取消海外投资者持有美债的利息所得税，消除主权基金抛售美债、动摇美元体系根基的风险。
+- **财政影响**：关税收入每年约3000–4000亿美元可覆盖额外支出，赤字率基本维持5–6%，不会大幅扩张；短期7–9月财政部发债约1万亿美元带来流动性抽水，但幅度或不及2023年（当时推高美债利率从3.8%至5%）。
+## 关税
+- **实施判断**：关税大概率实施，因需支撑每年3000–4000亿美元收入；需维持当前约10%的豁免税率水平，过高则通胀受不了，威胁高税率或为谈判技巧。
+- **有效税率**：当前约10–12%，若8月1日全回去甚至提高，回到10–15%，最极端约18%；对通胀路径不构成大幅改变，年底通胀约3.3–3.4%。
+- **谈判进展**：时间变相延后（原定7月9日未达成），相比4月2日对等关税水平大部分回落；加拿大、墨西哥、欧盟因贸易占比高需单独谈妥，其他国家即便增加一倍对有效税率影响很小。
+- **对华关税**：约40–50%，需关注8月12日中美谈判进展，尤其越南、英国协议均含转口限制（越南转口限制40%），需密切跟踪。
+## 港股流动性
+- **流动性判断**：7–9月美元流动性供给压力叠加港币汇率7.84–7.85、金管局需回收流动性，三季度流动性供给不如二季度；但美元美债利率非绝对主导变量，自身基本面强可盖过影响。
+- **市场状态**：港股指数在23000–24000区间震荡；分红股短期透支（银行股溢价已低于20%，扣税后股息率优势收窄），长期仍具相对国债利率优势。
+- **布局方向**：成长端拥挤度下降，创新药、人形机器人、AI应用、短视频生成、软件等中期有催化剂，建议在合适位置提前布局长期正确板块。
+## 光伏反内卷
+- **政策升级**：6月29日起人民日报发声剖析光伏行业现状，7月1日中财委第6次会议提出依法依规治理低价无序竞争、推动落后产能退出，7月3日工信部召开光伏企业座谈会传达党中央重视程度与破除反内卷迫切性。
+- **整合判断**：硅料环节集中度高（在产企业不到20家）、成本曲线最陡峭（颗粒硅现金成本约28元/公斤，尾部厂商高达45元/公斤）、供需比超200%，整合最为迫切；电池组件分散、整合相对困难。
+- **价格企稳**：多晶硅期货价格已触及40元/公斤，现货报价上周大幅上涨（前一周约35元），硅片报价涨约10%、电池涨约2分钱，组件涨幅相对靠后约10%；光伏玻璃协会呼吁降产保价，7月计划降产30%，需出清约2万吨方可修复供需平衡。
+## 人形机器人
+- **三季度主线**：围绕华为云生态开放、本土人形机器人企业技术闭环、特斯拉延期带来的硬件替代窗口期三大主线展开。
+- **华为链**：华为发布盘古世界模型与CloudRobot平台，构建多模态生成、规划、执行三大能力，明确不造机器人、以RTC方式开放，有望探索AI agent或license收费模式。
+- **本土企业**：智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿元、下半年有望加速上市；两家中标中国移动约1.2亿元人形机器人采购订单，部署于营业厅与消费者互动。
+- **特斯拉硬件替代**：Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案并筛选供应商；轻量化（以塑代钢等）与电机散热优化成为共性瓶颈突破方向。
+## 游戏板块
+- **政策环境**：今年1月和3月国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门政策支持包；6月版号单月发放158个（国产147个、进口11个），为2018年以来单月最高水平。
+- **市场景气**：2025年1–5月游戏市场规模同比增长17%（1400多亿元），手游同比增长20%；自2024年8月以来单月持续正增长。
+- **新品周期**：中型厂商新品成为核心催化，吉比特《仗剑传说》首月流水2亿多元、巨人网络《超自然行动组》6月流水过亿；大厂缺少大体量产品，对中型厂商获客友好。
+- **估值判断**：当前TTM PE约30倍、2025年静态PE约20倍，低于2023年AI行情45倍；新品利润有滞后性、明年兑现，在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击。
 # Q&amp;A环节
-**问**：大美丽法案对美股、美债、美元及港股流动性具体有什么影响？
-**刘刚凯文**：大美丽法案三大块内容：提高债务上限约5万亿美元，消除违约风险；延长2017年减税法案，每年额外支出约3400亿美元、总计3.4万亿美元；取消899条款，避免海外投资者抛售美债。关税收入每年约3000-4000亿美元可覆盖额外支出，财政赤字率维持在5-6%。三季度美债供给增加约1万亿美元，可能推高美债利率，但幅度或不及2023年（3.8%-5%），美元流动性边际收紧。港股流动性三季度不如二季度，港币汇率在7.84-7.85，金管局可能收紧流动性。结论是美股美债波动提供再配置机会，不悲观；港股流动性边际收紧但非主导变量。
-**问**：关税政策有哪些新变化？对通胀和美联储降息有何影响？
-**刘刚凯文**：关税有效税率当前约10-12%，极端情况回到18%。对等关税后大部分国家税率回落，除巴西外。加拿大、墨西哥、欧盟贸易占比高，需重点关注。对华关税约40-50%，越南转口限制40%，8月12日中美谈判需关注转口限制。通胀年底可能升至3.3-3.4%，但不大幅改变路径。美联储7月降息勉强，9月后可能降息。关税大概率是谈判技巧，市场静观其变，对通胀影响可控。
-**问**：光伏行业反内卷政策进展如何？哪些环节最值得关注？
-**刘佳妮**：全球新增光伏装机从2020年130GW增至2024年530GW，CAGR 42%，2025-2026年需求增速预计回落至10%左右，2025年全球需求预计650-700GW，电池产能为需求1.5倍，硅片组件2倍，硅料2.5倍。2022年以来产业链价格下跌70-90%，硅片电池2023Q4亏损，硅料组件2024Q2亏损。政府反内卷政策升级，2025年6月29日起高层连续发声，7月1日中财委会议，7月3日工信部座谈会，但具体措施未披露。硅料环节集中度高，现金成本差异大，颗粒硅28元/公斤，尾部厂商45元/公斤，硅料整合最迫切；光伏玻璃第二轮产能出清，7月计划降产30%，需出清约2万吨；多晶硅期货价格触及40元/公斤，现货价格上周大幅上涨。光伏行业底部企稳，头部一体化企业穿越周期能力强。
-**问**：人形机器人三季度有哪些投资主线？
-**郭文秀**：二季度A股机器人板块下跌约9%，跑输机械设备12个百分点，特斯拉4月宣布量产时间线延后叠加关税影响降低风险偏好。6月底华为发布盘古世界模型和CloudRobot平台，支持点云和视频双模态；智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿元，智元、宇树中标中国移动约1.2亿元人形机器人采购订单。特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案。港股机器人板块二季度估值溢价明显，下半年有确定性扩容。建议关注三条主线：华为云生态、本土企业技术闭环、特斯拉硬件替代，以及三类信号：华为云生态接入、头部企业出货量跨越500台/1000台、电机硬件优化。
-**问**：游戏板块调整后是否还有配置机会？
-**张雪琴**：游戏板块上涨接近两三个月，上周初开始调整。6月版号单月发放158个（国产147个，进口11个），2018年以来最高；2025年1-5月游戏市场规模同比增长17%，手游同比增长20%。今年缺乏大厂大作，但中型厂商新品成为核心催化，如吉比特《仗剑传说》首月流水2亿多，巨人网络《超自然行动组》6月流水过亿。当前游戏板块TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍。新品利润有滞后性，明年兑现。政策支持力度空前，游戏行业逆周期性。游戏板块调整后有望再次实现戴维斯双击，当前是配置时间点。</t>
+**问**：大美丽法案对港股流动性和外围资金流向有什么影响？
+**刘刚凯文**：7—9月美债供给压力确定，美元流动性边际收紧，叠加港币汇率在7.84—7.85、金管局需回收流动性，三季度港股流动性供给不如二季度，IPO融资较多也形成约束。但美元和美债利率不是主导港股的唯一变量，自身基本面强可以盖过其影响，单变量上略微偏负面。港股指数过去一两个月在23000—24000区间震荡，上不去也未必下得来。
+**问**：关税谈判的最新进展如何？对通胀和美联储降息有什么影响？
+**刘刚凯文**：关税大概率要做，需维持当前约10%的豁免税率才能收上来3000—4000亿美元以支撑支出；税率不能太高，否则通胀受不了，所以市场逐渐脱敏、静观其变。新变化是时间变相拖后（原定7月9日未达成），相比4月2日对等关税水平大部分回落，除巴西外没有大幅增加；加拿大、墨西哥、欧盟贸易占比高需单独谈妥，其他国家即便增加一倍也不影响有效税率。当前有效税率约10—12%，极端情况回到18%。通胀压力缓慢抬升，年底约3.3—3.4%，不大幅改变通胀路径，美联储7月降息勉强，9月及四季度之后仍可降。对华关税约40—50%，需关注8月12日中美谈判进展及转口限制。
+**问**：光伏反内卷政策具体有哪些动作？哪些环节最容易整合？
+**刘佳妮**：政策级别在提升：6月29日人民日报发声《在破除内卷式竞争中实现高质量发展》，指出光伏高投入低产出、阶段性供需错配等问题；7月1日中财委第六次会议提出依法依规治理企业低价无序竞争、推动落后产能退出；7月3日工信部召开光伏企业座谈会，指出技术创新和产能升级是反内卷重要手段。目前未见具体干预措施披露。硅料环节最易切入整合：集中度高（在产企业不到20家）、成本曲线最陡峭（颗粒硅现金成本约28元/公斤，尾部国内厂商可达45元/公斤）、供需比超200%为各环节最高，且作为最上游影响全产业链定价。下游电池和组件较分散，整合相对困难。
+**问**：光伏行业价格和供需现状如何？哪些企业能穿越周期？
+**刘佳妮**：2025年全球需求预计650—700GW，硅料产能是需求2.5倍、硅片组件2倍、电池1.5倍；2022年以来产业链价格下跌70%—90%，硅片电池自2023年四季度亏损、硅料组件自2024年二季度亏损，目前未见企业退出。政策预期下多晶硅期货价格已触及40元/公斤，现货价格上周较前一周35元左右大幅上涨，硅片报价涨约10%、电池涨约两分钱，组件涨幅相对靠后约10%。光伏玻璃协会呼吁降产保价，7月计划降产30%，需出清约2万吨方可修复供需平衡。穿越周期能力强的企业：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流；低杠杆、强现金、融资能力强的企业财务压力小；持续技术创新（颗粒硅使用比例从10%—20%提升到50%、硅片薄片化、铜替代银等）可逆势获得市场份额。
+**问**：人形机器人三季度有哪些催化剂和投资主线？
+**郭文秀**：三季度围绕三条主线：一是华为云生态开放，6月底华为开发者大会首发盘古世界模型，支持点云和视频双模态同时生成，CloudRobot平台构建多模态生成、规划、执行三大能力，华为明确不造机器人、以RTC方式开放，未来有望探索AI Agent或License收费；二是本土企业技术闭环，智元机器人拟通过收购材料厂商在A股上市，宇树科技年收入突破10亿元、下半年有望加速上市，两家同时中标中国移动约1.2亿元人形机器人采购订单；三是特斯拉延期带来的硬件替代窗口，Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案和筛选供应商，轻量化（以塑代钢）是解决续航的方向。建议关注三类信号：华为云生态接入厂商三季度继续新增、头部企业出货量跨越年化500台或1000台、电机硬件优化对应的窗口。
+**问**：游戏板块这波调整是结束还是回调后可以上车？
+**张雪琴**：我们的态度旗帜鲜明是后者。当前TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍。今年1—5月游戏市场规模同比增长17%、手游同比增长20%，6月版号单月发放158个（国产147个、进口11个）为2018年以来最高。中型厂商新品成为核心催化，吉比特《仗剑传说》首月流水2亿多元、巨人网络《超自然行动组》6月流水过亿，对其利润提升可达50%以上。新品利润有滞后性，今年上线的新品利润更多要到明年兑现，所以表观估值不便宜，但明年业绩确定性提供了坚实基础。在消费、政策和新品周期三重利好下，游戏板块有望在调整后再次实现戴维斯双击。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>100.4</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22868/9926</t>
+          <t>22868/8445</t>
         </is>
       </c>
     </row>
@@ -3872,83 +3876,68 @@
       <c r="C10" t="inlineStr">
         <is>
           <t># 课程概况
-本节主题班会以“梦想”为核心，由主讲老师（发言者2）主持，面向全班同学展开。课程围绕五个大点进行：老师先以丑小鸭变白天鹅的寓言引入，并分享个人追梦经历——高中立志考中国美术学院，单考已过但因离家远、家庭经济原因未去，最终入读广东技术师范大学（原民族学院）；大学期间保持专业排名第一（专业共41人），并实现加入学生会、参加比赛、考取教师资格证等梦想。随后通过“梦想观察团”游戏，播放航模爱好者何宗发（中国唯一去法国巴黎比赛，计划明年世界锦标赛再比高下）和普通歌手（唱歌走调可通过后天学习调整）的视频，引导学生讨论实现梦想的条件。老师强调实现梦想需要坚持、努力、勇敢、机会、兴趣、能力和学习等条件，并以马云为例说明起点低但坚持可成功。最后，老师展示自己的梦想之路（读书到考大学经历11年，录取优秀班干部用2年，获得国家励志奖学金用1年，成为优秀人民教师待定），并让学生写下个人梦想清单，建议梦想可列清单、实现后打勾，强调梦想要量力而行、可调整目标，先定小目标再定大目标。
+本节主题班会围绕“梦想”展开，由老师（发言者 2）主持。老师先询问同学们的梦想，学生积极发言，如当保安、当喜剧人、当太空人、当世界冠军等。老师分享个人追梦经历：曾梦想考中国美术学院，单考已过但因离家远、家庭经济原因未去，后就读广东技术师范大学（原广东民族学院），大学期间保持专业排名第一（专业共41人）、加入学生会并参与举办新生晚会、参加校运会等比赛、考取教师资格证，最终因定向师范政策回到龙川县任教。老师播放视频展示航模爱好者何聪发和普通歌手追梦的故事，引导学生讨论实现梦想的条件，总结实现梦想需要坚持、努力、勇气、机会、兴趣、能力和学习等条件，强调不要嘲笑任何人的梦想，机会留给有准备的人。老师以马云为例（中考两次、高考多次，最终成为中国首富），说明梦想可以逐步调整和实现，建议将大梦想分解为小目标。老师要求学生写下自己的梦想清单并收齐，学生分享的梦想包括考试考到630分、成为设计师、大学四年攒20万、成为创业者、成为光荣的人民教师等，老师给予鼓励和总结，强调每个梦想都值得尊重，鼓励学生坚持并努力实现。
 # 核心知识点梳理
 ## 梦想的定义与价值
-- **梦想的含义**：老师以“丑小鸭想变成白天鹅”引出梦想主题，指出梦想是个人追求的目标，每个梦想都值得尊重。
-- **梦想的普遍性**：老师提问班级同学梦想，学生回答包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等，老师指出“想当太空人”的广告词深入人心。
-- **不被嘲笑的梦想**：老师引用“不被嘲笑的梦想不是梦想”，强调即使梦想被嘲笑也要坚持，如自己高中立志考中国美术学院时曾被嘲笑。
-- **梦想的独特性**：老师指出“每一个人的梦想都是不可以复制的，都是独一无二的”，并以马云为例说明梦想不可复制。
+- **班会主题引入**：老师以“梦想”为主题开场，询问全班同学的梦想，学生积极发言，回答包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等。
+- **梦想值得尊重**：老师强调“每一个梦想都是值得我们尊重的”，并引用“不被嘲笑的梦想不是梦想”，鼓励学生不要因他人嘲笑而放弃梦想。
+- **梦想可以调整**：老师建议梦想可一步步调整，如先考进年级前百，再定前50的目标，逐步向大目标靠近；梦想清单列得越多，实现的几率越大。
+- **梦想需要坚持**：老师以马云为例，指出其中考两次、高考多次，最终成为中国首富，说明“一个人的起点高还是低不重要，看的是你能不能坚持”。
 ## 实现梦想的条件
-- **坚持与努力**：老师强调实现梦想需要坚持和努力，引用“天赋只是1%”的说法，指出唱歌走调可通过后天学习调整。
-- **勇敢与行动**：老师表扬班上同学勇敢站上讲台唱歌，指出实现梦想需要勇气去行动。
-- **机会与准备**：老师强调“机会都是留给有准备的人”，实现梦想需要机会，但机会需要提前准备。
-- **兴趣、能力与学习**：老师指出兴趣、能力以及学习都是实现梦想的必备条件，缺一不可；具备所有条件会**更快**实现梦想。
-- **条件缺失的影响**：老师引导学生讨论“缺少一个条件梦想是否还能实现”，小结为缺少某些条件梦想仍可能实现，但具备所有条件会加速实现。
-## 教师个人追梦案例
-- **高中梦想**：老师高中时立志考中国美术学院，单考已过，曾在国旗下讲话当着全校面宣布此梦想，当时被嘲笑。
-- **大学选择**：老师因离家远和家庭经济原因未去中国美术学院，选择定向生政策入读广东技术师范大学（原民族学院），定向生免学费，毕业后回龙川县教书。
-- **定向生限制**：老师说明定向生**不能考研**，但可在职考研，需边工作边读研且学费自费。
-- **大学成就**：老师大学期间保持本专业排名第一（专业共41人），实现加入学生会、参加比赛、考取教师资格证等梦想。
-- **梦想之路时间线**：老师展示个人梦想之路：读书到考大学经历**11年**，录取优秀班干部用**2年**，获得国家励志奖学金用**1年**，成为优秀人民教师**待定**。
-## 梦想观察团案例
-- **航模爱好者何宗发**：视频展示何宗发为中国唯一去法国巴黎比赛的航模选手，梦想带飞机环游世界、把中国国旗挂在世界赛场上，表演飞机有真实原型机歼10，计划在明年世界锦标赛再比高下。
-- **普通歌手案例**：视频展示普通人在宿舍练习唱歌，即使唱歌走调也可通过后天学习调整，最终可能成为歌手。
-- **观察团讨论**：老师组织4个大组作为“梦想观察团”，观察航模小伙子和想成为歌手的普通人，讨论实现梦想需要的条件。
-- **视频启示**：老师总结视频内容，强调不要嘲笑任何人的梦想，尽管现在在睡觉也好，顶峰相见。
-## 梦想清单制定方法
-- **清单步骤**：老师示范梦想清单写法：第1个是什么、第2个是什么、第3个是什么，实现后给清单打勾，并思考实现所需时间及实现后的收获。
-- **分阶段调整**：老师建议梦想可一步步立高，如先定考进年级前百，再定前50；实现不了可调整目标，量力而行。
-- **学生梦想示例**：学生分享的梦想包括：考试不犯糊涂、考上重本211、成为医学专业学生、成为设计师、大学4年攒20万、考630分、家人平安、世界和平、成为光荣的人民教师等。
-- **梦想收集安排**：老师要求每个小组第1个同学收集本组同学的梦想清单，在班会课结束时交给老师。
-## 马云案例与梦想启示
-- **马云追梦经历**：老师介绍马云中考考了两次才考上高中，高考考了多次，现成为中国首富，说明起点高低不重要，关键在能否坚持。
-- **马云新梦想**：老师引用马云的话，过去15年中国因他们而改变，希望未来15年世界因他们而改变，马云享受改变他人的乐趣。
-- **梦想的延续**：老师以航模小伙子为例，梦想实现后可以立得更高，从中国走向全世界，梦想可以一步步提高。
+- **核心条件**：老师总结实现梦想需要**坚持、努力、勇气、机会、兴趣、能力和学习**等条件，其中“学习、坚持、行动”是梦想条件中必不可少的三个。
+- **机会留给有准备的人**：老师强调“机会永远都是留给有准备的人”，并指出如果缺少某一个条件，梦想仍有可能实现，但具备所有条件会**更快实现**。
+- **不要嘲笑他人梦想**：老师播放视频展示航模爱好者何聪发和普通歌手追梦的故事，指出唱歌走调可通过后天学习调整，因此“不要去嘲笑任何一个人的梦想”。
+- **勇气与行动**：老师表扬班上一位同学在同学起哄下仍勇敢站上讲台唱歌，鼓励学生要有勇气去行动。
+## 老师的个人追梦经历
+- **高中梦想**：老师高中时曾在国旗下讲话，当着全校的面立志考上中国美术学院，当时被很多人嘲笑；单考已过，但因离家远、家庭经济原因未去就读。
+- **大学经历**：老师就读于广东技术师范大学（原广东民族学院），大学期间保持本专业排名第一（专业共41人），加入学生会并参与举办新生晚会，参加校运会等比赛，考取教师资格证。
+- **定向师范选择**：老师因定向师范政策（本科六年、免学费）回到龙川县任教，当时因不情愿哭了三天，但如今认为听从父母选择是正确的，且越来越喜爱教师行业。
+- **梦想之路时间线**：老师分享自己的梦想之路——考上大学用了11年，录取优秀班干部用了2年，获得国家励志奖学金用了1年，成为优秀人民教师待定。
+## 梦想清单的制定
+- **清单格式**：老师要求学生拿出纸写下梦想清单，内容包括：第1个梦想、第2个梦想、第3个梦想等，实现后可以打勾，并思考实现梦想需要的时间以及实现后的收获。
+- **学生梦想示例**：学生分享的梦想包括考试考到630分、成为设计师、大学四年攒20万、成为创业者、成为光荣的人民教师、家人平安、世界和平、祖国越来越好等。
+- **梦想可大可小**：老师指出梦想可以只写一个，也可以制定多个；先定小目标再定大目标，实现不了时可量力而行、调整目标。
+- **收齐方式**：老师要求每个小组第1个同学收齐本组同学的梦想清单并交给老师。
 # 课堂互动与答疑
 **学生**：老师，您的梦想是什么？
-**教师**：我的梦想是成为受学生喜爱的、有名望的优秀人民教师，目前还在努力过程中。
-**学生**：老师，您以前想考中国美术学院，为什么最后没去？
-**教师**：单考已过，但因离家远和家庭经济原因未去，最终入读广东技术师范大学（原民族学院），走定向师范路线，毕业后回龙川县教书。
+**教师**：我的梦想是成为受学生喜爱的、有名望的优秀人民教师，目前仍在努力过程中。
+**学生**：老师，您以前想考中国美术学院，后来实现了吗？
+**教师**：单考已过，但因离家远、家庭经济原因未去就读，后入读广东技术师范大学（原广东民族学院），定向回龙川县任教。
 **学生**：定向生可以考研吗？
-**教师**：定向生不能在校读研，但可在职考研，需边工作边读、学费自费。
-**学生**：老师，您大学是怎么保持专业排名第一的？
-**教师**：专业共41人，我大学四年保持排名第一，靠的是每天5点起床、坚持自律。
-**学生**：实现梦想需要哪些条件？
-**教师**：需要坚持、努力、勇敢、机会、兴趣、能力和学习；机会留给有准备的人，具备所有条件会加速梦想实现。
-**学生**：缺少一个条件，梦想还能实现吗？
-**教师**：缺少某个条件，梦想仍有可能实现；但条件都具备时，实现会更快。学习、坚持、行动是必不可少的三个条件。
-**学生**：马云中考、高考都考了好几次，为什么还能成功？
-**教师**：起点高低不重要，关键在能否坚持。马云中考两次才考上高中，高考多次，现已成为中国首富。
-**学生**：马云的新梦想是什么？
-**教师**：过去15年中国因他们而改变，希望未来15年世界因他们而改变，他享受改变他人的乐趣。
-**学生**：如果考不进年级前50怎么办？
-**教师**：可先把梦想调整为考进前百，考进后再定前50，一步步往前进，梦想要量力而行、可调整。
+**教师**：定向生不能在校读研，但可在职考研，边工作边读研，学费自理。
+**学生**：老师，您大学怎么保持专业排名第一？
+**教师**：每天坚持5点起床，大学四年保持本专业41人中排名第一，靠的是自律与坚持。
+**学生**：实现梦想需要什么条件？
+**教师**：需要坚持、努力、勇气、机会、兴趣、能力和学习；机会留给有准备的人，缺一条件梦想仍可能实现，但条件齐备会加速实现。
+**学生**：如果梦想实现不了怎么办？
+**教师**：可以调整目标，如先考进年级前百再冲前50，一步步往前进；梦想还是要有的，万一实现了呢。
+**学生**：马云中考两次、高考多次，为什么还能成功？
+**教师**：起点高低不重要，关键在能否坚持；马云新梦想是让世界因他们而改变，他享受改变他人的乐趣。
 # 课后任务与学习建议
 ## 课堂练习
-- **梦想观察团游戏**：全班分4个大组，各为一观察团，观看航模爱好者何宗发与普通歌手追梦视频，找出实现梦想所需条件，讨论缺少任一条件梦想是否还能实现。
-- **梦想清单写作**：学生拿出纸写下自己的梦想，可仿照老师示例列清单（第1个、第2个、第3个……），实现后打勾，并思考实现所需时间及实现后的收获。
-- **梦想清单分享**：写完后由每个小组第1个同学收集本组梦想清单交给老师，老师当堂展示并点评部分学生梦想。
+- **梦想观察团活动**：全班分4个大组，各为一观察团，观察航模爱好者何聪发与想当歌手的普通人两个对象，讨论实现梦想需要具备的条件，各组代表发言。
+- **梦想清单写作**：学生拿出纸写下自己的梦想清单，按老师示范格式列第1个、第2个、第3个梦想，并写明实现所需时间及实现后的收获，写完后由每组第1位同学收齐交给老师。
+- **梦想分享与点评**：老师当堂展示并点评学生梦想清单，如考试考到630分、成为设计师、大学四年攒20万、成为创业者、成为光荣的人民教师等，逐一给予鼓励。
 ## 复习重点
-- **实现梦想的条件**：坚持、努力、勇敢、机会、兴趣、能力、学习；机会永远留给有准备的人，学习、坚持、行动是梦想条件中必不可少的三个。
-- **梦想可调整**：目标实现不了时可量力而行、调整目标，如先定考进年级前百，再定前50，一步步往前进。
-- **梦想分阶段**：梦想可列清单分阶段实现，先定小目标再定大目标，制定多个梦想实现几率更大。
-- **不嘲笑他人梦想**：每个梦想都值得尊重，唱歌走调可通过后天学习调整，不被嘲笑的梦想不是梦想。
-- **梦想之路示例**：老师读书到考大学经历11年，录取优秀班干部用2年，获得国家励志奖学金用1年，成为优秀人民教师待定。
+- **实现梦想的条件**：坚持、努力、勇气、机会、兴趣、能力和学习，缺一不可；具备全部条件可加速实现梦想，其中学习、坚持、行动是必不可少的三个条件。
+- **机会留给有准备的人**：机会是实现梦想的条件之一，但只有提前准备、持续积累的人才能抓住机会。
+- **梦想可调整**：目标实现不了时可量力调整，如先考进年级前百再考进前50，一步步往前进；梦想也可以从小的目标逐步立高，如航模爱好者从国内舞台走向世界锦标赛。
+- **不嘲笑他人梦想**：每个梦想都值得尊重，唱歌走调可通过后天学习调整，不要嘲笑任何人的梦想，顶峰相见。
+- **梦想需要坚持**：以马云为例，中考两次、高考多次，最终成为中国首富，说明起点高低不重要，关键在能否坚持。
 ## 学习建议
-- **制定梦想清单**：仿照老师示例，用漂亮纸张写下自己的梦想，按第1个、第2个、第3个列清单，实现后打勾，并标注实现所需时间与收获。
-- **分阶段设定目标**：梦想可先定小目标再定大目标，如先考进年级前百再定前50；目标实现不了时量力而行、及时调整。
-- **坚持与行动**：实现梦想需坚持努力并付诸行动，如老师大学4年保持专业排名第一（专业41人），每天5点起床学习。
-- **勇敢尝试**：像班会中主动上台唱歌的同学一样，即使被起哄也勇敢站上讲台；想当歌手的同学可在班会课结束时自愿上台演唱。
-- **收集与分享**：每个小组第1个同学负责收集本组同学的梦想清单并交给老师，老师当堂点评分享，梦想写得实在、诚恳一点。</t>
+- **制定梦想清单**：仿照老师示范，列出多个梦想并编号，实现后打勾；每个梦想写明所需时间与收获，梦想可多列也可只定一个，多列实现几率更大。
+- **分解大目标为小目标**：将大梦想拆解为可逐步达成的小目标，如先考进年级前百再冲刺前50，一步步向前推进。
+- **勇敢行动**：像班内同学一样，即使被起哄也勇敢站上讲台唱歌；有梦想就要付诸行动，不要只停留在想法。
+- **坚持自律**：老师大学4年保持专业排名第一（专业共41人），靠的是每天5点起床的自律与坚持，可借鉴其作息与学习节奏。
+- **抓住机会并持续学习**：机会留给有准备的人，平时注重兴趣培养与能力提升；老师因定向师范政策回龙川任教，说明选择与机会结合的重要性。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>50.9</v>
+        <v>48.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9362/3640</t>
+          <t>9362/3116</t>
         </is>
       </c>
     </row>
@@ -4123,89 +4112,86 @@
       <c r="C11" t="inlineStr">
         <is>
           <t># 全文摘要
-本期新闻联播由央视播音员播报，围绕国内发展成就与国际动态展开，涵盖文化自信与改革、赵乐际访俄、夏粮丰收、铁路货运、快递业、油气管网、防汛及国内联播快讯等板块。习近平总书记提出将中华优秀传统文化精华与马克思主义立场观点方法相结合，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。全国人大常委会委员长赵乐际于7月9日至13日访俄，会见普京并出席中俄议会合作委员会第九次会议，俄方表示坚定恪守一个中国原则。今年夏粮产量达2996亿斤创历史新高，6月国家铁路发送货物3.32亿吨，上半年快递业务量超800亿件，预计全年新增油气管网里程超4000公里。国际方面，特朗普竞选集会遭未遂刺杀，以军空袭加沙致90人死亡。
+本期新闻联播由央视播音员播报，围绕国内发展成就与国际动态展开。国内方面，报道了文化自信与中华民族现代文明建设、赵乐际访问俄罗斯、夏粮产量创历史新高、6月份铁路货运指标增长、上半年快递业发展提速、油气管网建设提速、渝川皖等地应对降雨天气等新闻；国际方面，涵盖多国人士评价中国改革成就、特朗普竞选集会遭未遂刺杀、以军空袭加沙致90人死亡、黎以冲突、俄乌冲突及加拿大林火等事件。关键结论包括：文化体制改革取得历史性成就，文化自信明显增强；中俄立法机构将深化合作，落实两国元首共识；夏粮首战告捷，为全年粮食丰收奠定基础。全篇重要数字锚点：夏粮产量2996亿斤、铁路货运量3.32亿吨、快递业务量800亿件、油气管网输气能力增幅48%、以军空袭致90人死亡。
 # 分段速览
 ## 00:00-08:31 文化自信与中华民族现代文明建设
-本段为新闻联播开篇专题，系统阐述党的十八大以来文化体制改革成就。习近平总书记提出将中华优秀传统文化精华与马克思主义立场观点方法相结合，并在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时强调传承弘扬中华优秀传统文化。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。中央审议通过《深化文化体制改革实施方案》和《关于实施中华优秀传统文化传承发展工程的意见》，文化领域供给侧结构性改革深入推进，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力新引擎。
-## 08:31-12:39 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
-全国人大常委会委员长赵乐际应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。赵乐际在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。今年是中俄建交75周年，双方表示将从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作。沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
-## 12:39-14:21 夏粮产量创历史新高
-今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。主产区一、二等小麦占比普遍较高，小麦质量为近年来最好水平，夏粮首战告捷为全年粮食丰收奠定坚实基础。
-## 14:21-16:03 铁路货运与快递业发展提速
-国铁集团数据显示，6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高。化肥农药运量同比增长26.2%，增幅最大；中欧班列6月开行1719列，发送货物18万标箱，同比分别增长15%、11%。上半年我国快递业务量超800亿件，快递企业已运行国际航线40余条，农村寄递网络覆盖范围逐渐扩大，每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件。
-## 16:03-19:12 油气管网建设提速
-今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%。到2025年将初步形成四大油气战略通道，建成“五纵五横”天然气干线管网。
-## 19:12-20:40 渝川皖等地应对降雨天气
-重庆28个区县出现暴雨，其中13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江出现内涝、滑坡等险情，消防救援人员转移被困群众；安徽滁州市全椒县加强巡堤，处置堤防渗漏和管涌。水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
-## 20:40-23:38 国内联播快讯
-北京上半年320个市区重大项目全部开工，总投资超过4000亿元；燕矶长江大桥北岸主塔封顶，主跨1860米，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道；第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军；内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底；“中非儿童手拉手”活动在京启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将赴北京、河南参观访问。
-## 23:38-30:27 国际新闻
-多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放为世界提供更广阔市场和发展机遇。美国前总统特朗普在宾夕法尼亚州竞选集会遭未遂刺杀，右耳中枪受伤，一名观众死亡、两名受重伤，枪手被特勤局狙击手击毙。以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法；以军还袭击黎巴嫩多个边境村镇，叙利亚首都大马士革遭空袭。俄军打击乌军列车点，乌军击退俄军进攻；加拿大东北部林火蔓延，9600人被疏散。
+本段为新闻联播开篇专题报道，系统回顾党的十八大以来文化体制改革成就。习近平总书记提出将中华优秀传统文化精华与马克思主义立场观点方法相结合，并在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时强调传承弘扬中华优秀传统文化。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。报道还提及《深化文化体制改革实施方案》《关于实施中华优秀传统文化传承发展工程的意见》等文件，以及文化领域供给侧结构性改革、文旅融合、非遗保护、公共文化服务体系建设等进展。
+## 08:39-12:31 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
+全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与联邦委员会主席马特维延科、国家杜马主席沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。双方就落实两国元首重要共识、深化立法机构合作、巩固政治互信等交换意见。沃洛金表示俄坚定恪守一个中国原则。访问期间，赵乐际向俄无名烈士墓敬献花圈。
+## 12:49-14:21 夏粮产量创历史新高
+报道今年夏粮生产情况，强调夏粮作为全年粮食生产第一仗的重要性。夏粮生产克服多重自然灾害影响，单产实现恢复性增长，小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高。中央深入推进“藏粮于地、藏粮于技”战略，为提单产发挥重要作用。
+## 14:28-16:03 铁路货运与快递业发展
+国铁集团数据显示6月份国家铁路货运多项指标创历史同期新高，重点物资运输保障有力，境内运输网络更加完善，中欧班列国际联运量质齐升。上半年我国快递业务量超800亿件，国际运输能力稳步增强，农村寄递网络覆盖范围扩大，快递业不断丰富服务场景、拓展服务领域。
+## 17:29-19:12 油气管网建设提速
+今年以来我国油气管网基础设施加速建设，西气东输四线已完成吐鲁番至中卫段主体管道工程建设，川气东送二线、虎林到长春天然气管道等工程加速推进。我国能源供应与保障能力进一步提升，按照规划到2025年将建成“五纵五横”天然气干线管网。
+## 19:20-20:40 渝川皖等地应对降雨天气
+重庆、四川、安徽等地出现强降雨天气，当地组织工作人员连夜抢险排涝、转移被困群众、加强巡堤并处置堤防险情。水利部针对“七下八上”防汛关键期逐流域安排防御，联合调度上游干支流水库群减小三峡水库入库洪峰流量。
+## 20:41-23:38 国内联播快讯
+本段为多条国内新闻简讯，包括北京上半年320个市区重大项目全部开工、燕矶长江大桥北岸主塔封顶、第二十三届环青海湖国际公路自行车赛收官、内蒙古第34届草原那达慕开幕、“中非儿童手拉手”活动在京启动等。
+## 23:47-30:27 国际新闻与地方改革成就
+多国人士高度评价中国全面深化改革扩大开放成就。国际方面报道了特朗普竞选集会遭未遂刺杀、以军空袭加沙地带致90人死亡、以军袭击黎巴嫩边境村镇、叙利亚大马士革遭空袭、俄乌冲突及加拿大林火等事件。节目最后介绍上海、浙江全面深化改革、扩大开放，在推进中国式现代化建设中走在前列。
 # 要点梳理
 ## 文化自信与中华民族现代文明建设
-- **理论创新**：习近平总书记提出把中华优秀传统文化精华与马克思主义立场、观点、方法相结合，强调“我们五千年的文明，我们要尊重，也要弘扬”。
+- **理论指引**：习近平总书记提出要把中华优秀传统文化精华与马克思主义立场、观点、方法结合起来，指出这是中国特色社会主义。
 - **重要会议**：2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述“两个结合”尤其是“第二个结合”的重大意义；2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。
-- **实地考察**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院指出一定要把真理本土化；在三苏祠强调汲取治国理政理念和思维；在武夷山朱熹园提出以时代精神激活中华优秀传统文化生命力。
-- **制度文件**：《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署。
-- **文化事业成就**：深入实施中华文明探源工程、高标准推进国家文化公园建设；中国共产党历史展览馆、国家版本馆等文化地标落成；《复兴文库》、“中国历代绘画大系”出版。
-- **文化产业数据**：我国成为图书、电视剧、动漫等领域生产大国；数字文化产业成为激发消费潜力“新引擎”；电影市场规模屡创新高。
+- **实地调研**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院指出一定要把真理本土化；在三苏祠强调汲取治国理政理念和思维；在武夷山朱熹园提出以时代精神激活中华优秀传统文化生命力。
+- **制度文件**：《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。
+- **文化成就**：我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高；深入实施中华文明探源工程，推进国家文化公园建设，中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版。
 ## 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
-- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日对俄罗斯进行正式友好访问；在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。
-- **中俄关系定位**：今年是中俄建交75周年；在两国元首战略引领下，中俄新时代全面战略协作伙伴关系高水平、高质量发展。
+- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议；访问期间在莫斯科向俄无名烈士墓敬献花圈。
+- **中俄关系定位**：今年是中俄建交75周年，在两国元首战略引领下，中俄新时代全面战略协作伙伴关系高水平、高质量发展。
 - **赵乐际表态**：中国全国人大愿同俄罗斯联邦会议从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献；要以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持。
 - **普京表态**：俄中立法机构始终保持高水平合作，有助于在立法层面推进双边合作的优先议题；加强俄中议会合作委员会工作有利于两国交流经验、互学互鉴，促进立法、地方等各领域合作。
-- **马特维延科表态**：发展对华关系得到俄社会广泛认同和支持；两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流。
-- **沃洛金表态**：俄国家杜马不同党派在发展对华关系上高度一致；俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
-- **中俄议会合作委员会第九次会议**：赵乐际10日出席并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作等五点主张。
-- **其他行程**：访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
+- **马特维延科表态**：发展对华关系得到俄社会广泛认同和支持，两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流。
+- **沃洛金表态**：俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
+- **中俄议会合作委员会第九次会议致辞要点**：密切战略协作服务中俄关系发展大局；交流治国理政经验助力各自国家发展振兴；发挥立法机构职能作用以法治方式促进务实合作；传承弘扬传统友谊夯实国家关系社会和民意基础；加强多边协作从立法机构层面团结壮大“全球南方”力量。
 ## 夏粮产量创历史新高
-- **总产量**：今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮生产克服多重自然灾害影响。
-- **单产数据**：夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤；单产恢复性增长是夏粮产量增加的主要原因。
-- **政策支撑**：中央深入推进“藏粮于地、藏粮于技”战略；全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金。
-- **质量亮点**：小麦质量为近年来最好水平；主产区一、二等小麦占比普遍较高；夏粮首战告捷为全年粮食丰收奠定坚实基础。
-## 6月份国家铁路货运指标
+- **产量数据**：今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩375.2公斤，小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。
+- **政策支撑**：中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。
+- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，得益于集成技术推广应用、科学防灾减灾、收割晾晒及时。
+- **总体评价**：夏粮首战告捷为全年粮食丰收奠定坚实基础。
+## 6月份国家铁路货运多项指标稳定增长
 - **总体数据**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
 - **重点物资**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量均创历史同期新高。
-- **境内运输网络**：连接内陆物流节点城市的多式联运快车已覆盖各省会城市；连接港口和内陆腹地城市的铁海快线班列已覆盖全国主要港口。
+- **境内网络**：连接内陆物流节点城市的多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口。
 - **国际联运**：6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
-## 上半年快递业发展
+## 上半年我国快递业发展提速
 - **业务总量**：截至6月30日，今年我国快递业务量已达800亿件。
-- **国际运输**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；多地启用、升级跨境仓。
-- **农村网络**：每天超1亿多件快递包裹在农村地区流动；5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。
+- **国际运输**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，在多地启用、升级跨境仓。
+- **农村网络**：每天超1亿多件快递包裹在农村地区流动，农村寄递网络覆盖范围逐渐扩大。
+- **业务高峰**：5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。
 - **融合发展**：快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
-## 油气管网建设
-- **年度目标**：预计全年新增管道里程超4000公里，“全国一张网”不断完善。
-- **重点工程**：西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
-- **管网现状**：我国主干油气管网约10万公里；输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%；天然气“全国一张网”日供气能力超10亿立方米。
-- **2025年规划**：初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网。
-## 渝川皖等地应对降雨天气
-- **重庆雨情**：7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨；当地组织工作人员连夜抢险排涝。
-- **四川险情**：暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。
-- **安徽汛情**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌。
-- **水利部部署**：针对“七下八上”防汛关键期即将到来和雨情水情形势逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程；水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+## 我国油气管网建设提速“全国一张网”不断完善
+- **建设规模**：预计全年新增管道里程超4000公里；西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
+- **供应能力**：主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。
+- **未来规划**：到2025年将初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网。
+## 渝川皖等地积极应对降雨天气
+- **重庆**：7月13日8时至14日8时，九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝。
+- **四川**：暴雨造成内江部分地区内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。
+- **安徽**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌。
+- **水利部调度**：针对“七下八上”防汛关键期逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
 ## 国内联播快讯
-- **北京重大项目**：上半年北京市计划新开工的320个市区重大项目已全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超过4000亿元。
-- **燕矶长江大桥**：7月14日北岸主塔封顶，下一步转入主缆施工阶段；大桥连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
-- **环青海湖国际公路自行车赛**：7月14日在海北州门源县收官，经过8天8个赛段，国内外22支车队154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
-- **内蒙古草原那达慕**：第34届于7月14日在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
-- **“中非儿童手拉手”活动**：7月14日由外交部、全国妇联主办，在中国儿童中心启动；来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问。
+- **北京重大项目**：上半年计划新开工的320个市区重大项目全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超4000亿元。
+- **燕矶长江大桥**：北岸主塔封顶，下一步转入主缆施工阶段；大桥连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
+- **环青海湖国际公路自行车赛**：第二十三届赛事在海北州门源县收官，经过8天8个赛段，国内外22支车队154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
+- **内蒙古草原那达慕**：第34届在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
+- **“中非儿童手拉手”活动**：由外交部、全国妇联主办，在中国儿童中心启动；纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问。
 ## 国际新闻
-- **多国人士评价中国改革**：多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量；中国推进深层次改革和高水平开放，为世界提供更广阔的市场和发展机遇。
-- **特朗普竞选集会遭未遂刺杀**：13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击；特朗普在社交媒体称右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众受重伤；枪手从集会现场外高处向演讲台“开了数枪”，所处屋顶距演讲台约180多米到270多米，开枪后被特勤局狙击手打死；美联邦调查局称特朗普遭未遂刺杀，正展开调查，枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明。
-- **以军空袭加沙马瓦西地区**：13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人，约300人受伤，死伤者包括许多妇女和儿童；以色列总理内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马，今后将继续发动类似袭击；哈马斯表示袭击使局势“严重升级”；巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明予以谴责。
-- **加沙地带其他冲突**：以军13日在拉法、加沙城等地打击巴武装人员和军用设施；巴武装派别同日使用迫击炮、火箭弹等打击以军阵地和坦克等目标。
-- **黎以边境冲突**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因以军白磷弹袭击发生火灾；黎巴嫩真主党武装声明打击了位于以色列北部的以军集结地及情报设施。
-- **叙利亚遭空袭**：叙利亚军方7月14日称，大马士革卡夫苏萨地区等多个地点凌晨遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
-- **俄乌冲突**：俄罗斯国防部13日称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌克兰武装部队总参谋部称乌军当天与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
-- **加拿大林火**：13日纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大目前正应对500多起活跃林火，其中超400起处于失控状态。</t>
+- **多国人士评价中国改革**：高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量；中国推进深层次改革和高水平开放为世界提供更广阔的市场和发展机遇。
+- **特朗普竞选集会遭未遂刺杀**：13日在美国宾夕法尼亚州巴特勒市竞选集会发生枪击，特朗普称右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众受重伤；枪手从集会现场外高处向演讲台“开了数枪”，所处屋顶距演讲台约180多米到270多米，开枪后被特勤局狙击手打死；美联邦调查局称特朗普遭未遂刺杀，正展开调查，枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明。
+- **以军空袭加沙马瓦西地区**：13日空袭加沙南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者包括许多妇女和儿童；以色列总理内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马，今后将继续发动类似袭击；哈马斯表示袭击使局势“严重升级”；巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明予以谴责；以军13日还在拉法、加沙城等地打击巴武装人员和军用设施，巴武装派别使用迫击炮、火箭弹打击以军阵地和坦克。
+- **以军袭击黎巴嫩边境村镇**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾，多处房屋被毁；黎巴嫩真主党武装打击了以色列北部的以军集结地和情报设施。
+- **叙利亚遭空袭**：14日凌晨大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
+- **俄乌冲突**：俄军使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌军当天在前线地区与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
+- **加拿大林火**：东北部纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大目前正应对500多起活跃林火，其中超400起处于失控状态。</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>70.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7755/6449</t>
+          <t>7755/5764</t>
         </is>
       </c>
     </row>
@@ -4444,135 +4430,135 @@
       <c r="C12" t="inlineStr">
         <is>
           <t># 课程概况
-本节课为初中几何光学复习课，由主讲人系统梳理光的直线传播、光的反射、镜面反射与漫反射、平面镜成像及球面镜应用五大板块，并结合例题讲解巩固。课程首先介绍几何光学历史与光源、光线概念，强调光在均匀介质中沿直线传播，列举三点一线、激光准直、小孔成像、日食月食、影子形成等实例，并给出光在真空中的速度为3×10⁸米/秒（约每秒绕地球赤道7圈半），在空气中略慢，在水中约为真空的3/4，在玻璃中约为2/3。光的反射定律部分，主讲人明确三线共面、分居两侧、反射角等于入射角，强调垂直入射时入射角与反射角均为0度，并讲解作图步骤。平面镜成像部分，说明成像原理为光的反射定律，成等大、正立的虚像，像与物关于镜面对称，并分析实验误差原因。球面镜部分，凸面镜发散光线，应用于汽车后视镜；凹面镜会聚光线，应用于手电筒、太阳灶等，并提及玻璃幕墙光污染问题。
+本节课为初中几何光学复习课，主讲人系统梳理了光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用等核心知识，并通过例题讲解与课堂练习巩固各知识点。光的直线传播部分介绍了光源（自然光源与人造光源）与光线（物理模型）概念，强调光在均匀介质中沿直线传播，列举三点一线、激光准直、小孔成像、日食月食、影子形成等实例，并给出光在真空中的传播速度为3×10⁸米/秒。光的反射定律部分强调三线共面、分居两侧、反射角等于入射角，并讲解入射角与反射角的计算及作图方法。镜面反射与漫反射部分区分了两者特点，指出黑板反光属于镜面反射、电影银幕产生漫反射，两种反射均遵守反射定律。平面镜成像部分讲解成像原理为光的反射定律，成像是正立、等大、虚像，像与物连线垂直镜面、像距等于物距，并分析实验误差原因。球面镜部分介绍凸面镜发散光线、凹面镜会聚光线及其应用实例。
 # 核心知识点梳理
 ## 光的直线传播
-- **几何光学定位**：初中阶段光学（直线传播、反射、折射）统称几何光学，人类从2000多年前古希腊时期就开始研究，当时哲学家已找到直线传播和反射规律；高中阶段才讲光的干涉、衍射等更复杂内容。
-- **光源定义**：自身能够发光的物体；按来源分为**自然光源**（如太阳）和**人造光源**（如火把、蜡烛、煤油灯、电灯），按形状可分为点光源和平行光源。
-- **光线概念**：用一条带有箭头的直线代表光线，是**物理模型**，并非真实存在；画太阳这类从无限远处来的光源时用一束平行光表示。
-- **光沿直线传播条件**：光在**均匀介质**中沿直线传播；大气层不均匀会使光线发生偏折，如太阳越出地平线、星星眨眼睛都是大气层不均匀造成的。
-- **三点一线实例**：步枪瞄准练习时眼睛看到瞄准点、准心尖和标尺缺口三者重合即认为在一条直线上，原理是光在均匀介质中沿直线传播；队列排齐、木工师傅闭一只眼看尺子是否平直同理。
-- **激光准直**：利用激光沿直线传播的特性进行准直，是现代常用方法。
-- **小孔成像**：光沿直线传播的实例，成**倒立实像**（光线实际到达），放大缩小不一定，与孔形状无关；《墨经》中有记载，因此考试常考。
-- **小孔成像实验**：纸杯底部用针扎小孔（不能用钉子杵大孔），前面用塑料布蒙上，点燃蜡烛放在小孔前方，可在塑料布上看到火苗倒立的像；夏天大杨树底下晃动的光斑就是太阳透过树叶缝隙形成的小孔成像，因太阳距地球远大于树叶缝隙到地面距离，得到的是太阳缩小的像，且因角度不一定正，光斑常呈椭圆形。
-- **日食形成**：太阳、月球、地球在同一直线上，**月球在中间**；1号区域发生**日全食**，2、3号区域发生**日偏食**，4号区域发生**日环食**；日全食时月球把太阳全挡住，该区域全黑。
-- **月食形成**：太阳、地球、月球在同一直线上，**地球在中间**；月球完全在地球阴影（1号区域）内发生**月全食**；月球部分在1号区域、部分在2或3号区域时才发生**月偏食**——若月球只在2、3号区域，只是比正常情况略暗，不叫月偏食。
-- **影子形成**：影子（俗称阴影）的形成也是光沿直线传播的实例，中国唐朝的皮影戏利用了这一原理。
-- **光速数值**：光在真空中的传播速度为 `3×10^8` 米/秒（即 `3×10^5` 千米/秒，约每秒30万公里），**一秒钟绕地球赤道7圈半**。
-- **光速在不同介质中**：空气中约 `2.99×10^8` 米/秒，比真空中略慢（近似处理）；水中约为真空中的 `3/4`；玻璃中约为真空中的 `2/3`。
-- **光速计算题**：激光从地球射到月球表面用时1.25秒，按真空光速计算，距离 `s = V×T = 3×10^8 × 1.25 = 3.75×10^8` 米。
-- **声光对比**：发生雷电时先看到闪电后听到雷声，因为**光速比声速快**；声速在15℃时约 `340` 米/秒，远慢于光速。
+- **光源定义**：自身能够发光的物体，分为自然光源（如太阳）和人造光源（如火把、蜡烛、煤油灯、电灯）。
+- **光线概念**：用带箭头的直线表示，是**物理模型**，并非真实存在；按来源分为自然光源与人造光源，按形状分为点光源与平行光源。
+- **传播规律**：光在均匀介质中沿直线传播；大气层不均匀会使光线发生偏折，如太阳越出地平线、星星眨眼睛。
+- **三点一线**：步枪瞄准时眼睛、准心尖、标尺缺口三者重合，依据光在均匀介质中沿直线传播；队列排齐、木工看尺子是否平直同理。
+- **激光准直**：利用激光沿直线传播进行准直。
+- **小孔成像**：成**倒立实像**，放大缩小不一定，与孔形状无关；依据《墨经》记载，是中国人最早的研究成果；生活中树荫下的光斑即太阳通过树叶缝隙的小孔成像，是缩小的实像。
+- **日食**：太阳、月球、地球在同一直线上，月球在中间；1号区域为日全食，2、3号区域为日偏食，4号区域为日环食。
+- **月食**：太阳、地球、月球在同一直线上，地球在中间；月球完全在地球阴影内为月全食，部分在1号区域、部分在2或3号区域才出现月偏食；月球在2、3号区域只是略暗，不叫月偏食。
+- **影子形成**：光在均匀介质中沿直线传播的实例，如唐朝皮影戏。
+- **光速**：真空中为 `3×10^8` 米/秒（`3×10^5` 千米/秒），一秒钟绕地球赤道7圈半；空气中略慢（约 `2.99×10^8` 米/秒），水中约为真空中的3/4，玻璃中约为真空中的2/3。
+- **光速计算**：激光从地球射到月球表面时间1.25秒，距离为 `3.75×10^8` 米（`s=V×T`）。
+- **声光对比**：先看到闪电后听到雷声，因光速比声速快；声速15℃时为340米/秒。
 ## 光的反射定律
-- **基本概念**：入射光线AO射到平面镜上，O为入射点，反射光线为OB；**法线**是垂直于镜面的辅助线（虚线，真实不存在），也是角AOB的角平分线；入射角是入射光线与法线的夹角，反射角是反射光线与法线的夹角。
-- **反射定律三句话**：① 反射光线、入射光线和法线在**同一平面内**（三线共面）；② 反射光线和入射光线**分居法线两侧**；③ **反射角等于入射角**。
-- **引入法线的原因**：为后面学习光的折射做准备，不能直接用入射光线与镜面的夹角来定义。
-- **易错点**：光垂直射到镜面上时，入射角和反射角都是 **0度**（不是90度），因为入射角按定义是入射光线与法线的夹角。
-- **作图步骤**：① 先画法线（虚线，画两三段断开即可，保留作图痕迹）；② 根据反射角等于入射角找到对应角度；③ 画出入射或反射光线并补全箭头；可用尺子刻度对称法（如法线对准20刻度，反射光上找5厘米点，入射侧找对称的5厘米点）快速作图，不必用量角器。
-- **例题**：反射光线与平面镜夹角40度，则入射角为 `90° - 40° = 50°`；入射光线与法线夹角60度时反射角60度；反射光线与入射光线夹角80度时反射角40度（角平分线）。
-- **入射角变化规律**：入射光线与镜面夹角增大时，入射角减小，反射角也减小，传播速度不变。
+- **定律内容**：反射光线、入射光线和法线在同一平面内（共面）；反射光线和入射光线分居法线两侧；反射角等于入射角。
+- **法线引入**：法线是垂直于镜面的辅助线，画虚线，真实不存在；引入法线是为后续学习折射做准备。
+- **易错点**：光垂直射到镜面上时，入射角和反射角均为**0度**（不是90度）；反射光线与平面镜夹角40度时，入射角为50度。
+- **作图步骤**：先画法线（虚线，两三段即可），再根据反射角等于入射角确定光线，最后补全箭头；作图痕迹（法线）要保留。
+- **例题结论**：入射光线与镜面夹角增大时，入射角减小，反射角也减小，传播速度不变；反射光线与入射光线夹角80度时，反射角为40度。
 ## 镜面反射与漫反射
-- **镜面反射**：平行光射到光滑表面（平面镜、平静水面、光滑金属表面），各入射点法线平行，反射光线平行射出；人眼只有在特定位置才能看到反射光，否则看不到。
-- **漫反射**：平行光射到凹凸不平的表面，把每个小面看作小平面镜分别画法线，反射光线射向各个方向，人眼在任何位置都能看到；**生活中大多数反射是漫反射**（黑板、电影银幕、人的皮肤等）。
-- **共同点**：镜面反射和漫反射**都遵守光的反射定律**。
-- **黑板反光**：教室某些位置看黑板只看到一片光亮而看不清粉笔字，是黑板对光发生了**镜面反射**；电影放映机射到银幕上的光经幕布反射进入人眼，是**漫反射**（银幕白色且粗糙）。
-- **雨后水潭判断**：雨后夜晚，**迎着月光走**，地面上发亮处是水潭（水面发生镜面反射）；**背着月光走**，地面上发暗处是水潭。
-- **家庭实验**：白纸上放一面小镜子，手电筒光垂直照在镜子上，斜着看镜子是黑的、周围白纸是亮的——镜子发生镜面反射光线回去了，白纸表面粗糙发生漫反射。
-- **光路可逆**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明在平面镜中的像，原理是**光路可逆**。
+- **镜面反射**：平行光射到光滑表面，反射光平行，人眼在特定位置才能看到；如商场玻璃隔断易使人撞上。
+- **漫反射**：平行光射到凹凸不平表面，反射光射向各个方向，人眼在任何位置都能看到；生活中大多数反射是漫反射，如黑板、电影银幕、人的皮肤。
+- **黑板反光**：教室某些位置看到一片光亮而看不清粉笔字，是黑板对光发生镜面反射。
+- **电影银幕**：白色荧幕粗糙，使射到屏幕上的光发生漫反射，电影院、教室黑板、投影幕布同理。
+- **雨后水潭**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭；可用白纸放小镜子、手电筒垂直照射验证——斜看镜子是黑的，白纸是亮的。
+- **共同规律**：镜面反射和漫反射都遵守光的反射定律。
+- **光路可逆**：小明能看到小刚在平面镜中的像，则小刚也一定能看到小明在平面镜中的像。
 ## 平面镜成像
-- **成像原理**：平面镜成像依据**光的反射定律**，反射光线的反向延长线会聚形成像点S′，实际光线并未到达像的位置，因此成的是**虚像**。
-- **成像特点**：成**正立、等大、虚像**；像与物的连线**垂直镜面**；像到镜面的距离**等于**物到镜面的距离（像与物关于镜面对称）。
-- **实验器材与目的**：用**玻璃板**代替平面镜（便于移动后面的蜡烛确定像的位置）；用**刻度尺**比较像与物到镜面的距离；用**两段完全相同的蜡烛**比较像与物的大小。
-- **光屏验证**：用光屏（毛玻璃、白塑料片、白墙等）放在像的位置，**不能接收到烛焰的像**，因为实际光线没有到达，证明成的是虚像；若将物体靠近玻璃板，像的大小**不变**。
-- **实验误差原因一**：蜡烛到玻璃板的距离与像到玻璃板的距离不相等，原因是**玻璃板与水平面不垂直**（或与事先画好的镜面位置没有重合）。
-- **实验误差原因二**：在玻璃板同一侧看到同一个蜡烛的两个像，原因是**玻璃板有厚度**，它的两个面都能发生反射成像；玻璃板越薄（如3毫米）两个像越难区分，厚玻璃板（如8毫米）则明显看到两个像。
-- **视力表例题**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子 **1.5米** 即可看到5米处的虚像；若视力表距镜子3米，人距镜子2米即可。
-- **人与像距离**：人站在平面镜前1米处，人与像之间的距离为 **2米**；人向远离平面镜方向移动，镜中的像大小**不变**。
-- **水中倒影辨析**：人在河边看到岸边树在水中的倒影属于光的反射（平静水面充当平面镜），成的是正立等大的虚像，只是文学上习惯称“倒影”；人在河边看到河水深度比实际浅是光的**折射**现象。
-- **易混点**：平面镜成的是正立等大的虚像，与小孔成像成倒立实像不同。
+- **成像原理**：光的反射定律，成像是虚像。
+- **成像特点**：**正立、等大、虚像**；像与物连线垂直镜面，像距等于物距。
+- **实验器材**：用玻璃板代替平面镜，便于确定像的位置；刻度尺用于比较像与物到镜面的距离；两段完全相同的蜡烛用于比较像与物大小。
+- **光屏验证**：光屏（白塑料片、毛玻璃、白墙）不能接收到烛焰的像，因实际光线未到达；物体靠近玻璃板时，像的大小不变。
+- **实验误差原因**：玻璃板与水平面不垂直（或未与预先画好的镜面位置重合）；玻璃板有厚度，两个面发生反射成像，造成看到两个像。
+- **视力表应用**：视力表距镜子3.5米，像距镜子也3.5米，人距镜子1.5米即可看到5米处的虚像；若视力表距镜子3米，人距镜子2米即可。
+- **距离计算**：人站在平面镜前一米处，人与像距离2米；人远离平面镜时，像的大小不变。
+- **水中倒影**：平静水面充当平面镜，树在水中的倒影是正立、等大的虚像，文学上称「倒影」易与平面镜成像混淆。
 ## 球面镜及其应用
-- **凸面镜**：对光线起**发散作用**，成正立、缩小的虚像；应用于**汽车后视镜**、丁字路口转弯处的镜子、停车场拐角镜。
-- **凹面镜**：对光线起**会聚作用**，平行光反射后会聚于焦点F；应用于**手电筒**（电珠小灯泡放在焦点处）、**汽车前大灯**、**探照灯**、**太阳灶**（西藏藏民用铝合金金属板做太阳灶烧水）、**耳鼻喉科检查**（医生戴凹面镜，中间镂空以便观察，光汇聚在耳道、鼻道、嗓子眼）。
-- **以直代曲原则**：讨论凸面镜、凹面镜作图时，把曲面看作许多小平面镜的组合，这是物理上“以直代曲”的方法。
-- **阿基米德传说**：敌人船队来犯时，阿基米德让妇女们把梳妆镜（平面镜）组织起来围成凹面，把光线汇聚烧毁敌人帆船。
-- **玻璃幕墙光污染**：玻璃幕墙做成凹面会汇聚光线，可能烧死树木（学校为保留老枣树特意用玻璃幕墙做凹面走廊，结果树被烧死）、引燃电线（焦点正好落在电线上导致电线自燃）；还会反射声音造成噪音，属于**光污染**隐患。
-- **凸面镜视觉差异**：司机看后视镜时觉得车离得并不近，因为凸面镜成的是缩小的像，视觉上有差异。
+- **凸面镜**：对光线起**发散作用**，成正立、缩小的虚像；应用于汽车后视镜、丁字路口反光镜；司机看后视镜感觉车距与实际有差异。
+- **凹面镜**：对光线起**会聚作用**，有焦点；应用于手电筒电珠（小灯泡在焦点处）、汽车前大灯、探照灯、耳鼻喉科检查镜、太阳灶。
+- **作图方法**：以直代曲，将曲面看作多个小平面镜处理。
+- **阿基米德传说**：用妇女梳妆镜围成凹面，汇聚光线烧毁敌人帆船。
+- **光污染风险**：玻璃幕墙凹面会聚光线可烧死树木（学校枣树三年被烧死）、引燃电线；凹面反射声音导致楼间噪音大。
 # 课堂互动与答疑
-**学生**：萤火虫算不算光源？
-**教师**：算，萤火虫自身能发光，属于自然光源；但实际照明效果有限，不能当学习用灯。
-**学生**：光线是真实存在的吗？
-**教师**：不是，光线是带箭头的直线，是物理模型，用来描述光的传播方向，实际并不存在。
-**学生**：小孔成像为什么一定是倒立的实像？
-**教师**：因为光沿直线传播，物体上各点发出的光通过小孔后交叉投射，所以像必然倒立；光线实际到达光屏，故为实像。放大缩小取决于物距与像距之比，与孔的形状无关。
-**学生**：月偏食是怎么形成的？
-**教师**：月球部分进入地球本影（1号区域）、部分处于半影（2、3号区域）时形成月偏食；若月球完全在本影中则为月全食，仅处于半影只会变暗，不叫月偏食。
-**学生**：光速在不同介质中一样吗？
-**教师**：不一样。真空中光速为3×10⁸米/秒（约每秒绕地球赤道7圈半）；空气中略慢，约2.99×10⁸米/秒；水中约为真空的3/4，玻璃中约为2/3。
-**学生**：光垂直射到镜面上，入射角是多少？
-**教师**：入射角是0度，不是90度。入射角定义为入射光线与法线的夹角，垂直入射时光线与法线重合，故入射角为0度，反射角也为0度。
-**学生**：画反射光线时一定要用量角器量角度吗？
-**教师**：不需要。先画法线（虚线，留作图痕迹），再用刻度尺在法线两侧找对称点，连接入射点即可，不必精确量角。
-**学生**：为什么用玻璃板代替平面镜做成像实验？
-**教师**：玻璃板既能反射成像又能透光，便于在后方移动另一支蜡烛确定像的位置；若用不透明平面镜则无法操作。
-**学生**：光屏为什么接收不到平面镜成的像？
-**教师**：因为平面镜成的是虚像，实际光线没有到达镜后，只是反射光线的反向延长线会聚形成的，所以光屏上接收不到。
-**学生**：实验中蜡烛到玻璃板的距离与像到玻璃板的距离不相等，原因是什么？
-**教师**：一是玻璃板与水平面不垂直，导致像的位置偏移；二是玻璃板有厚度，两个反射面分别成像，造成测量误差。
-**学生**：为什么透过玻璃板能看到同一个蜡烛的两个像？
-**教师**：因为玻璃板有厚度，前后两个表面都能发生反射成像；玻璃板越厚，两个像越明显，所以实验应选薄玻璃板。
-**学生**：平静水面的倒影为什么是正立的，却叫“倒影”？
-**教师**：平静水面充当平面镜，成的是正立、等大的虚像；所谓“倒影”是文学说法，实际像与物关于水面镜面对称，并非倒立。
-**学生**：凸面镜和凹面镜对光线各有什么作用？
-**教师**：凸面镜对光线起发散作用，成正立、缩小的虚像，用于汽车后视镜、丁字路口转弯镜；凹面镜对光线起会聚作用，用于手电筒、汽车前大灯、太阳灶、耳鼻喉科检查镜。
+**学生**：为什么研究反射时要引入法线，直接用量角器量入射光线和镜面的夹角不行吗？
+**教师**：只研究反射时确实可以不用法线，但后面学折射时，入射光线和折射光线不在镜面同侧，没有法线就无法统一描述角度关系。法线是人为引入的辅助线，实际不存在，所以画图时用虚线表示，它始终垂直于镜面，也是入射角与反射角的角平分线。
+**学生**：光垂直射到镜面上，入射角和反射角是多少？为什么不是90度？
+**教师**：入射角是入射光线与法线的夹角，垂直入射时入射光线与法线重合，夹角为0度，反射角也等于0度。容易错答成90度，是因为把入射角误当成入射光线与镜面的夹角了。
+**学生**：反射光线与平面镜夹角40度，入射角是多少？
+**教师**：入射角是入射光线与法线的夹角，法线垂直于镜面。光线与镜面夹角40度，则与法线夹角为90度减40度，即50度，反射角等于入射角，也是50度。
+**学生**：画反射光线或入射光线的作图题，步骤是什么？
+**教师**：第一步先过入射点画法线，法线用虚线且必须保留作图痕迹；第二步根据反射角等于入射角确定另一条光线的方向，可用刻度尺在法线两侧找对称点来保证角度相等；最后补全箭头。不需要用量角器精确测量，物理作图不要求数学上的精确度。
+**学生**：入射光线与镜面夹角增大时，反射角怎么变？
+**教师**：入射光线与镜面夹角增大，意味着入射光线向镜面方向偏转，入射角（与法线夹角）减小，反射角也随之减小，但传播速度不变。所以答案是反射角减小、传播速度不变。
+**学生**：镜面反射和漫反射有什么区别？为什么黑板反光时看不清字？
+**教师**：镜面反射是平行光射到光滑表面，反射光仍平行，只有特定位置的人眼能看到；漫反射是平行光射到凹凸不平的表面，每个小面都看作小平面镜，反射光射向各个方向，任何位置都能看到。黑板反光属于镜面反射，某位置反射光集中进入人眼形成亮斑，就看不清粉笔字了。两种反射都遵守光的反射定律。
+**学生**：雨后夜晚，迎着月光走和背着月光走，水潭分别看起来是亮还是暗？
+**教师**：水潭表面平静，发生镜面反射。迎着月光走时，月光经水面反射进入人眼，水潭发亮；背着月光走时，反射光射向另一侧，进入不了人眼，水潭发暗。地面粗糙发生漫反射，情况相反。判断依据是镜面反射的方向性。
+**学生**：平面镜成像实验为什么用玻璃板而不用镜子？
+**教师**：用镜子只能看到反射像，无法确定像的位置。玻璃板既能反射成像，又能透过它看到后面的蜡烛，便于移动未点燃的蜡烛去与像重合，从而确定像的位置并比较大小。
+**学生**：平面镜成像实验中，为什么用刻度尺和两段完全相同的蜡烛？
+**教师**：刻度尺用于比较像与物到镜面的距离是否相等；两段完全相同的蜡烛用于比较像与物的大小关系——后面的蜡烛与像完全重合，说明像与物等大。
+**学生**：平面镜成的像为什么是虚像？光屏能接收到吗？
+**教师**：平面镜成像的原理是光的反射，反射光线的反向延长线会聚形成像，实际光线并没有到达像的位置，所以是虚像，光屏接收不到。判断依据是实际光线是否到达：小孔成像是实际光线到达光屏，所以是实像。
+**学生**：平面镜成像实验中，测得像距和物距不相等，可能是什么原因？
+**教师**：两个原因：一是玻璃板与水平面不垂直，实验中玻璃板倾斜，像的位置偏移，导致测量不准；二是玻璃板有厚度，前后两个面都能反射成像，若玻璃板较厚，会看到两个像，影响测量。应选用薄玻璃板并确保其竖直放置。
+**学生**：为什么透过较厚的玻璃板会看到同一个蜡烛的两个像？
+**教师**：玻璃板前后两个表面都能发生反射，各自成一个像。玻璃板很薄时两个像几乎重合，肉眼分辨不出；玻璃板较厚（如8毫米）时，两个像明显分开，就能看到两个像。
+**学生**：平面镜成像有什么特点？为什么水中的倒影看起来是倒立的？
+**教师**：平面镜成的是正立、等大的虚像，像与物连线垂直镜面，像距等于物距。水中倒影是把平静水面当作平面镜，树在镜面中的像相对树本身是正立的，但相对观察者看起来是倒过来的，文学上叫倒影，实际仍是正立等大的虚像。
+**学生**：凸面镜和凹面镜对光线各有什么作用？分别用在哪些地方？
+**教师**：凸面镜对光线起发散作用，成缩小正立虚像，视野更大，用于汽车后视镜、丁字路口反光镜；凹面镜对光线起会聚作用，把平行光会聚到焦点，用于手电筒、汽车前大灯、太阳灶、耳鼻喉科检查镜。凹面镜会聚光线可产生高温，如玻璃幕墙凹面曾烧死树木、引燃电线。
 # 课后任务与学习建议
 ## 课堂练习
-- **第1–6题（光的直线传播）**：考点为光在均匀介质中沿直线传播及其实例。第1题答案即该原理；第2题影子和月全食均依据此原理；第3题激光从地球到月球用时1.25秒，按真空光速3×10⁸米/秒计算，距离为3.75×10⁸米；第4题选C；第5题多选选BCD，平面镜成像属反射而非直线传播；第6题选ABC，D项错在未强调均匀介质。
-- **第7题（反射定律探究实验）**：用带刻度硬纸板（中间用透明胶带粘合可前后转动）和小平面镜，配合激光笔验证反射定律；入射光线、反射光线与法线在同一平面内，反射角等于入射角。
-- **第8题（反射作图）**：方法为先画法线（虚线，画两三段即可），再根据反射角等于入射角确定另一条光线，补全箭头；作图痕迹保留法线即可，可用刻度尺对称取点法（如法线对准20刻度，反射光上取25处点，入射侧对应取15处点）快速作图。
-- **第9题**：反射光线与平面镜夹角40°，则入射角为50°，选A。
-- **第10题**：入射光线与镜面夹角增大时，入射角减小、反射角减小，传播速度不变，选C。
-- **第11题**：入射光线与法线夹角60°时，反射角为60°。
-- **第12题**：反射光线与入射光线夹角80°，反射角为40°（角平分线）。
-- **第13题（雨后水潭判断）**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭；选B、C。
-- **第14题（光路可逆）**：A错，垂直入射时反射角为0°而非90°；B对，小明能看到小刚在镜中的像，则小刚也一定能看到小明（光路可逆）；C错，漫反射同样遵守反射定律；D错，光在不同介质中速度不同。
-- **第15题**：电影院白色银幕对光产生漫反射，选B。
-- **第16题**：教室某些位置看黑板只见光亮看不清字，是黑板发生镜面反射；电影放映机射到银幕的光经幕布反射进入人眼，是漫反射；两种反射都遵守光的反射定律。
-- **第17题**：电影院白色屏幕粗糙，为使射到屏幕上的光发生漫反射。
-- **第18题**：属于光的反射的是D（人在河边看到岸边的树在水中的倒影）；A、B为直线传播，C为折射。
-- **第19题（平面镜成像实验误差分析）**：蜡烛到玻璃板距离与像到玻璃板距离不相等，原因一是玻璃板与水平面不垂直（或未与预先画好的镜面位置重合），原因二是玻璃板有厚度、两个面发生反射成像。
-- **第20题（平面镜成像实验）**：用玻璃板代替平面镜是为了便于确定像的位置；刻度尺用于比较像与物相对镜面的距离；两段完全相同蜡烛用于比较像与物大小；光屏不能接收到烛焰的像（虚像，实际光线未到达）；物体靠近玻璃板时像的大小不变。
-- **第21题**：视力表距镜子3.5米，像距镜子3.5米，人距镜子1.5米即可看到5米处的虚像。
-- **第22题**：视力表到镜距离改为3米，人到镜子2米即可，选B。
-- **第23题**：人站在平面镜前1米处，人与像之间距离为2米。
-- **第24题**：人向远离平面镜方向移动，镜中像的大小不变，选C。
+- **练习1–5（光的直线传播）**：考点为光在均匀介质中沿直线传播；影子和月全食均以此原理解释。激光从地球射到月球表面时间1.25秒，按真空光速3×10⁸米/秒计算，距离为3.75×10⁸米。
+- **雷电现象题**：先看到闪电后听到雷声，原因是光速比声速快；声速在15℃时约340米/秒，远小于光速。
+- **练习4（单选）**：选C。光在真空中沿直线传播；B项未说明真空条件，D项光在不同介质中速度不相同。
+- **练习5（多选）**：选BCD。平面镜成像属于光的反射，不属于直线传播实例。
+- **练习6（多选）**：选ABC。D项错在未强调均匀介质，光传播路线不一定为直线。
+- **练习7（反射定律探究实验）**：用带刻度的硬纸板（中间用透明胶带粘合、可前后转动）和小平面镜，用激光笔验证反射定律；此实验在家可用硬纸壳、胶带、小平面镜和激光笔完成。
+- **练习8（反射作图）**：先画法线（虚线，保留作图痕迹），再根据反射角等于入射角确定光线；可用刻度尺在法线两侧找对称点连线，最后补全箭头。
+- **练习9（单选）**：选A。反射光线与平面镜夹角40度，则与法线夹角为50度，入射角为50度。
+- **练习10（单选）**：选C。入射光线与镜面夹角增大时，入射角减小，反射角也减小，但传播速度不变。
+- **练习11**：入射光线与法线夹角为60度时，反射角为60度。
+- **练习12**：反射光线与入射光线夹角80度时，反射角为40度（角平分线关系）。
+- **练习13（雨后水潭判断）**：迎着月光走，发亮处是水潭（镜面反射）；背着月光走，发暗处是水潭。可用白纸上放小镜子、手电筒垂直照射验证：斜看时镜子黑、白纸亮。
+- **练习14（光路可逆）**：选B。小明能看到小刚在平面镜中的像，则小刚也一定能看到小明，依据是光路可逆；A项垂直入射反射角应为0度，C项漫反射同样遵守反射定律，D项光在不同介质中速度不同。
+- **练习15**：电影院白色银幕对光产生漫反射，选B。
+- **练习16**：教室某些位置看黑板只见光亮看不清粉笔字，是黑板发生镜面反射；电影放映机射到银幕的光经幕布反射进入人眼，是漫反射；两种反射都遵守光的反射定律。
+- **练习17**：电影院白色屏幕粗糙，为使射到屏幕上的光发生漫反射。
+- **练习18（单选）**：选D。人在河边看到岸边的树在水中的倒影属于光的反射（平静水面充当平面镜）；A、B为直线传播，C为光的折射。
+- **练习19（平面镜成像实验误差分析）**：蜡烛到玻璃板距离与像到玻璃板距离不相等，原因一是玻璃板与水平面不垂直（或未与预先画好的镜面位置重合），原因二是玻璃板有厚度，两个面发生反射成像。
+- **练习20（平面镜成像实验）**：用玻璃板代替平面镜是为了便于移动后面的蜡烛确定像的位置；刻度尺用于比较像与物到镜面的距离；两段完全相同的蜡烛用于比较像与物的大小；光屏不能接收到烛焰的像，因为平面镜成虚像，实际光线未到达后方；物体靠近玻璃板时，像的大小不变。
+- **练习21（查视力）**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子1.5米即可看到5米处的虚像，填1.5米。
+- **练习22（单选）**：选B。视力表到镜距离改为3米，像到镜距离也是3米，人到镜子2米即可。
+- **练习23**：人站在平面镜前1米处，人与像之间的距离为2米。
+- **练习24（单选）**：选C。人向远离平面镜方向移动，镜中像的大小不变。
 ## 复习重点
 - **光源**：自身能够发光的物体；按来源分为自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
-- **光线**：带有箭头的直线，是物理模型，并非真实存在；按形状可分为平行光源和点光源画法。
-- **光在均匀介质中沿直线传播**：适用条件为同一种均匀介质；实例包括三点一线瞄准、激光准直、小孔成像、日食月食、影子形成；大气层不均匀时太阳光发生偏折，故日出时太阳实际位置低于所见位置。
-- **小孔成像**：成倒立实像（光线实际到达光屏），放大缩小不一定，与孔形状无关；树荫下光斑是太阳经树叶缝隙形成的小孔成像，因太阳距地球远，得到的是太阳缩小的像。
-- **日食与月食**：日食时太阳、月球、地球在同一直线上，月球在中间，1号区域为日全食、2/3号区域为日偏食、4号区域为日环食；月食时地球在中间，月球完全进入1号区域为月全食，部分在1号区域、部分在2/3号区域才出现月偏食（仅处于2/3号区域只是略暗，不叫月偏食）。
-- **光速**：真空中为3×10⁸米/秒（3×10⁵千米/秒，约每秒绕地球赤道7圈半）；空气中略慢（约2.99×10⁸米/秒，常近似取真空值）；水中约为真空的3/4，玻璃中约为2/3；光速远大于声速（15℃时声速340米/秒），故先看到闪电后听到雷声。
-- **光的反射定律**：反射光线、入射光线和法线在同一平面内（三线共面）；反射光线和入射光线分居法线两侧；反射角等于入射角；垂直入射时入射角与反射角均为0°。
-- **法线**：过入射点垂直于镜面的辅助线，用虚线表示，是入射角与反射角的角平分线；引入法线是为后续折射学习作准备。
-- **镜面反射与漫反射**：镜面反射是平行光射到光滑表面后反射光平行，人眼仅在特定位置能看到；漫反射是平行光射到凹凸不平表面后反射光射向各个方向，人眼在任何位置都能看到；两者都遵守光的反射定律；生活中大多数反射是漫反射（黑板、电影银幕、人的皮肤）。
-- **平面镜成像**：原理为光的反射定律；成等大、正立的虚像；像与物连线垂直镜面，像距等于物距；光屏不能接收虚像（实际光线未到达）；平静水面、光滑金属表面可充当平面镜。
-- **凸面镜**：对光线起发散作用，成正立、缩小的虚像；应用于汽车后视镜、丁字路口转弯镜。
-- **凹面镜**：对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、太阳灶、耳鼻喉科检查镜；玻璃幕墙形成凹面会聚光线可能烧死树木、引燃电线，造成光污染。
+- **光线**：用带箭头的直线表示，是物理模型，并非真实存在；按形状可分为点光源（如蜡烛）和平行光源（如太阳光）。
+- **光在均匀介质中沿直线传播**：适用条件为同一种均匀介质；实例包括三点一线瞄准、队列排齐、木工看尺子是否平直、激光准直、小孔成像、日食月食、影子形成。
+- **小孔成像**：成倒立实像（光线实际到达），放大缩小不一定，与孔的形状无关；树荫下光斑是太阳通过树叶缝隙形成的小孔成像，因太阳距地球远大于缝隙距地面距离，得到缩小的像。
+- **日食与月食**：日食时太阳、月球、地球在同一直线上，月球在中间，1号区域为日全食、2/3号区域为日偏食、4号区域为日环食；月食时地球在中间，月球完全进入1号区域为月全食，部分在1号区域、部分在2/3号区域才出现月偏食（月球在2/3号区域只是略暗，不叫月偏食）。
+- **光速**：光在真空中传播速度为3×10⁸米/秒（约30万公里/秒），一秒钟绕地球赤道7圈半；空气中略慢（约2.99×10⁸米/秒），水中约为真空的3/4，玻璃中约为真空的2/3。
+- **光的反射定律**：反射光线、入射光线和法线在同一平面内（三线共面）；反射光线和入射光线分居法线两侧；反射角等于入射角。法线是垂直于镜面的辅助线，为后续折射学习作准备，真实不存在，画虚线。
+- **垂直入射特例**：光垂直射到镜面上时，入射角和反射角均为0度（不是90度），这是常见易错点。
+- **镜面反射**：平行光射到光滑表面，反射光平行，人眼在特定位置才能看到；商场玻璃隔断易使人撞上，黑板反光属此类。
+- **漫反射**：平行光射到凹凸不平表面，反射光射向各个方向，人眼在任何位置都能看到；生活中大多数反射为漫反射（黑板、电影银幕、投影幕布、人眼看到物体）。镜面反射和漫反射都遵守光的反射定律。
+- **平面镜成像原理与特点**：原理是光的反射定律；成像是正立、等大的虚像，像与物连线垂直镜面，像距等于物距；平静水面、光滑金属表面可充当平面镜。
+- **平面镜成像实验要点**：用玻璃板代替平面镜便于确定像的位置；刻度尺比较像与物到镜面距离；两段相同蜡烛比较像与物大小；光屏不能接收虚像；误差来源为玻璃板与水平面不垂直或玻璃板有厚度。
+- **凸面镜**：对光线起发散作用，成正立、缩小的虚像；应用于汽车后视镜、丁字路口反光镜。
+- **凹面镜**：对光线起会聚作用，应用于手电筒电珠（置于焦点）、汽车前大灯、探照灯、耳鼻喉科检查镜、太阳灶；阿基米德曾用凹面镜汇聚光线烧毁敌船。
+- **光路可逆**：光反射时光路可逆，小明能看到小刚在平面镜中的像，则小刚也一定能看到小明。
 ## 学习建议
-- **自制小孔成像实验**：用纸杯或易拉罐，底部用针扎小孔（勿用钉子杵大孔），前面用塑料布蒙上，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像；体会像与孔形状无关。
-- **自制反射定律探究装置**：用硬纸壳（中间用透明胶带粘合可前后转动）、小平面镜和激光笔，在纸壳上画好均匀刻度，即可在家验证反射定律。
-- **自制平面镜成像实验**：白纸上立一块透明玻璃板，用两支蜡烛（或两枚跳棋），一支点燃放在玻璃板前，移动另一支至看上去被点燃的位置，记录位置后可验证像与物连线垂直镜面、像距等于物距。
-- **观察光沿直线传播**：用激光笔对准直吸管照射墙面可见光点，弯折吸管后光点消失；也可在玻璃罩内点香或烟雾，用激光照射观察直线光路。
-- **观察镜面反射与漫反射**：白纸上放一面小镜子，用手电筒垂直照射，斜着看时镜子是黑的、周围白纸是亮的——镜子发生镜面反射光线返回，白纸发生漫反射。
-- **购买激光笔**：两元店或十元店即可买到装一节干电池的激光笔，光强度大、线直，适合完成直线传播、反射等实验。
-- **保护眼睛**：主讲人提醒长时间判卷、看屏幕、在日光灯下看书均费眼力，建议多到户外接触自然光，避免视力持续下降。</t>
+- **自制小孔成像实验**：用纸杯或易拉罐，底部用针扎小孔（不要用钉子扎大孔），前面用塑料布蒙上，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像；体会像与孔形状无关。
+- **自制反射定律探究装置**：用硬纸壳中间用透明胶带粘合（可前后转动），画上均匀刻度格，搁一块小平面镜，用激光笔照射即可在家验证反射定律。
+- **自制平面镜成像实验**：白纸上立一块透明玻璃，用两个蜡烛（或两枚跳棋子），移动后方未点燃蜡烛至看上去被点燃的位置，记录位置可验证像与物等大、等距、连线垂直镜面。
+- **购买激光笔**：两元店或十元店即可买到装一节干电池的激光笔，光强度大、线直，适合研究直线传播和反射实验；吸管实验：激光笔对准直吸管，墙上出现光点，弯折吸管后光点消失，证明光不会自行拐弯。
+- **观察生活中的光学现象**：夏天观察大杨树下的光斑（小孔成像，椭圆、缩小实像）；雨后夜晚判断水潭位置（迎着月光走亮处是水潭，背着月光走暗处是水潭）；用白纸和小镜子、手电筒验证镜面反射与漫反射的区别。
+- **保护眼睛**：主讲人提醒长时间判卷、看屏幕、拉窗帘上课都会损害视力，建议多到户外看远处，注意写字姿势，避免长时间盯屏幕。</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>80.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25691/8047</t>
+          <t>25691/7639</t>
         </is>
       </c>
     </row>
@@ -4683,106 +4669,102 @@
       <c r="C13" t="inlineStr">
         <is>
           <t># 课程概况
-本课程为电气工程基础，是电气专业学生进入专业课后的第一门入门课。主讲人提出两个教学目标：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及其与系统整体的关系，建立电力系统整体概念；二是掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术与计算方法。课程要求前修电路理论与电机学知识，特别是变压器和同步电机；后续重要课程包括电力系统分析、继电保护、电力系统自动化、高电压技术。本次讲授第1章，涵盖电力系统基本概念、特点、对系统的要求、电能质量指标及常用接地方式，并梳理了从直流输电早期试验到交流输电兴起、再到现代交直流并用的电力发展简史，讲解了电力系统、电力网、动力系统的定义，以及按规模划分的地方、区域、超高压远距离输送三类电网和变电站的分类方法。
+本课程为电气工程基础，是电气类专业进入专业课后的第一门入门课。课程教学目的有两个：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及其与电力系统整体的关系，建立电力系统的整体概念；二是掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术与计算方法。前修课程要求具备电路理论和电机学知识，特别是变压器和同步电机相关内容；后续重要课程包括电力系统分析、电力系统继电保护、电力系统自动化和高电压技术。本次课程为第一章导论，属全课程概念最多、最重要的章节，内容包括电力系统、电力网、动力系统、变电站等基本概念，电力系统的特点及要求，电能质量指标的国家标准规定范围，以及常用接地方式（中性点接地方式）。主讲人还梳理了从直流到交流的电力发展简史，说明三相三线制因效率最高、金属消耗量最小而占主导地位，并讲解了电力系统从单机供电到多机并联、升压远距离输电的形成过程，给出电力系统、电力网、动力系统的定义及地方、区域、超高压远距离三类电网的划分。
 # 核心知识点梳理
-## 课程定位与教学目标
-- **课程定位**：电气工程基础是进入专业课后的第一门课，属于专业入门课，对今后工作非常重要。
+## 课程教学目标与定位
+- **课程性质**：电气工程基础是进入专业课后的第一门课，属专业入门课，对今后工作非常重要。
 - **教学目标一**：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念。
-- **教学目标二**：掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术及基本计算方法。
-- **前修课程要求**：需了解电路理论和电机学知识，特别是**变压器和同步电机**相关知识要求较高，有欠缺的同学应课后补充。
-- **后续重要课程**：电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。
-## 第1章学习内容与难点
-- **基本概念**：学习电力系统、电力网、动力系统和变电站等相关概念。
+- **教学目标二**：掌握电力系统在分析、设计、运行、管理方面的最基础理论、基本技术及基本计算方法。
+- **前修课程**：要求对电路理论和电机学有一定了解，**特别是变压器和同步电机**相关知识要求较高；有欠缺的同学需自行补充相关内容。
+- **后续课程**：最重要的四门为电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。
+## 第一章学习内容与难点
+- **基本概念**：学习掌握电力系统、电力网、动力系统和变电站等若干基本概念。
 - **电力系统特点**：理解电力系统的特点，以及由特点引起的电力系统设计、运行等方面的基础理论。
 - **对电力系统的要求**：理解对电力系统提出的要求，涉及运行、设计和维护各个方面。
-- **电能质量指标**：掌握国家标准对电能质量指标的各种规定范围。
-- **常用接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地方式）的不同特点。
-- **难点一⭐**：由电力系统特点引出的基本原理，如**电能不能大量储存**决定了电力系统有功功率和无功功率的动态平衡问题，是运行调整和设计的基础。
-- **难点二⭐**：电力系统额定电压的规定繁杂，需把额定电压规定搞清楚。
-- **难点三⭐**：各种中性点接地方式直接影响后续多个章节内容，学习较困难。
-- **学习方法**：基本概念注意内涵和外延并适当记忆；从电力系统特点和要求出发、从最基础原理推导，不记结论；注意寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。
-## 直流输电发展简史
-- **早期直流试验**：1874年俄国工程师在彼得堡建成4.5公里直流输电线路，传输功率4.5千瓦，后用于有轨电车的原始工业试验。
-- **德普勒试验**：1882年法国德普勒架设首条57公里直流试验线路，采用电报线传输，首端电压1343伏、末端850伏，输送功率200瓦，损耗78%；1883年从法国南部进行14公里输电试验，输送功率1.1千瓦，损耗55%。
-- **直流三线制**：1882年10月英国科学家发明直流输电三线制系统，外线与中线间电压110伏、两外线间220伏，后扩展到5根线形成直流无限制系统。
-- **直流输电限制**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难，限制了直流远距离大容量输电。
-- **串联直流发电机**：19世纪末法国方剑将多台直流发电机串联以提高电压，将75千瓦电力输送75千米；20世纪初瑞典科学家加装短路器使任意发电机投切不停电，此后20多年建成15条直流输电线路。
-- **直流线路里程碑**：1906年法国慕尼黑水电厂至里昂180公里、57千伏、4700千瓦线路投运；1927年改建为260公里、125千伏、19000千瓦，接入两座水电站。
+- **电能质量指标**：掌握电能质量指标，包括国家标准对各项指标规定的范围。
+- **接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地方式）的不同特点。
+- **难点一 ⭐**：由电力系统特点引出的基本原理，如**电能不能大量储存**决定了有功功率和无功功率的动态平衡问题，是运行调整和设计的基础。
+- **难点二 ⭐**：电力系统额定电压的规定繁杂，需把额定电压规定搞清楚。
+- **难点三 ⭐**：各种中性点接地方式直接影响后续多个章节内容，学习较困难。
+- **学习方法**：注意基本概念的内涵和外延并适当记忆；从电力系统特点和要求出发、从最基础原理推导，不记结论；寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。
+## 直流输电发展史
+- **早期试验**：福泰勒用2000米导线连接瓦斯发电机，拖动直流电动机和水泵，证明直流远距离输电可行。
+- **1874年**：俄国工程师在彼得堡建成4.5公里直流输电线路，传输功率4.5千瓦，后用于有轨电车的原始工业试验。
+- **1882年**：法国德普勒架设首条57公里直流试验线路，采用电报线传输，首端电压1343伏、末端850伏，输送功率200瓦，**损耗78%**。
+- **1883年**：德普勒从法国南部进行14公里输电试验，输送功率1.1千瓦，损耗55%。
+- **1882年**：英国科学家发明直流三线制系统，外线与中线间电压110伏，两外线间220伏，后扩展为五线制。
+- **技术限制**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难，限制直流远距离大容量输电。
+- **串联升压尝试**：19世纪末法国方剑串联多台直流发电机，将75千瓦电力输送75千米；20世纪初瑞典科学家加装短路器实现不停电投切，此后20多年建成15条直流输电线路。
+- **最大直流线路**：1906年投运法国慕尼黑水电厂至里昂线路，180公里、57千伏、4700千瓦；1927年改建为260公里、125千伏、19000千瓦，接入两座水电站。
 - **直流输电局限**：设备复杂、运行方式复杂、造价高、可靠性差。
-## 交流输电发展简史
-- **变压器前身**：英国法拉第电磁感应原理；美国亨利用多匝线圈做原边、少匝线圈做副边，使高电压感应出低电压，是变压器前身。
-- **单相变压器**：1876年俄国科学家发明单相变压器，主要用于照明；法国和英国科学家联合将多台变压器串联到输电线路中，负荷变化时输电电压受干扰。
-- **感应电机与并联运行**：1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行方式，使并联运行成为可能。
-- **交直流之争**：爱迪生与凯尔文主张直流电，理由是直流电效率高、交流电有危险性（曾购买威斯汀豪斯交流发电机卖给监狱执行死刑以证明危险性）；威斯汀豪斯和特斯拉主张交流电，因交流电易用变压器升压降压、减少电能损失。
-- **交流输电示范**：1886年威斯汀豪斯在美国麻省进行1.2千米、30千伏交流输电示范；同年又在意大利建成17英里高压输电线路。
-- **三相交流发明**：1886年俄国科学家发明三相交流电、三相交流输电和三相异步电动机。
-- **交直流之争标志**：法国到德国的交流输电线路（被认为是第一条交流输电线路），水电厂安装三相发电机和升压变压器升压后送到德国，在法兰克福建两座降压变电站，一座供展览会照明，另一座供100马力三相异步电动机驱动人工瀑布离心泵。
-## 输电电压等级发展
-- **绝缘子与电压提升**：1898年发明针式绝缘子，美国加利福尼亚输电电压升至33千伏；1906年发明悬式绝缘子，建成110千伏高压输电线路。
-- **电晕与导线**：1912年发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成154千伏线路。
-- **均压阀技术**：1923年均压阀技术应用，成功建成220千伏输电线路。
-- **国际电压里程碑**：1936年美国287千伏线路投运；1952年瑞典建成380千伏线路，首次采用分裂导线；1956年苏联400千伏双回线路投运；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联1150千伏特高压线路投运，后降压至500千伏运行。
-- **国内电压里程碑**：1941年220千伏投运；1972年330千伏投运；1981年500千伏投运；2009年1000千伏交流特高压投运，是国家标志性首次投运成果。
-## 直流输电复兴与联网
-- **直流联网优势**：交流大电网稳定问题突出后，直流在联网中的优势逐渐显露，用于电网与电网之间的连接。
-- **海底电缆工程**：1954年瑞典本土与哥特兰岛建成世界首个工业采用海底电缆的直流工程，电压100千伏、96公里，采用汞弧阀换流。
-- **晶闸管换流阀**：1970年瑞典本土与哥特兰岛扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界首个晶闸管换流阀背靠背直流工程在加拿大投运。
-- **中国直流工程**：中国首个直流输电工程为舟山群岛与浙江定海电网连接；1989年葛上直流（葛洲坝电厂至上海）±500千伏；近期投运云广直流±800千伏特高压直流工程。
-## 三相交流输电优势
+## 交流输电发展史与交直流之争
+- **变压器前身**：英国法拉第电磁感应原理；美国亨利用多匝线圈作原边、少匝线圈作副边，使高电压感应出低电压。
+- **关键发明**：1876年俄国科学家发明单相变压器（主要用于照明）；1883年特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行方式。
+- **爱迪生与凯尔文主张直流**：理由为直流电效率高、交流电有危险性；曾购买威斯汀豪斯公司的交流发电机卖给监狱用于死刑犯执行，以证明交流危险。
+- **威斯汀豪斯与特斯拉主张交流**：交流电易用变压器升压降压，可在高电压下减少电能损失；交流发电机制造业发展为交流输电做了准备。
+- **交流输电示范**：1886年威斯汀豪斯在美国麻省进行1.2千米、30千伏交流输电示范；同年又在意大利建成17英里高压输电线路；1886年俄国科学家发明三相交流电、三相输电和三相异步电动机。
+- **交直流之争标志**：法国到德国的交流输电线路（常被认为第一条交流输电线路），水电厂装三相发电机和升压变压器升压后送电至德国，在法兰克福建两座降压变电站，一座供展览会照明，另一座供100马力三相异步电动机带动离心泵做人工瀑布。
+- **高压输电进展**：1898年发明瓷质绝缘子，美国加州输电电压升至33千伏；1906年发明悬式绝缘子，建成110千伏线路；1912年发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏线路。
+- **电压等级提升**：1936年美国287千伏投运；1952年瑞典建成380千伏线路，**首次采用分裂导线**；1956年苏联400千伏双回线路投运；1965年加拿大735千伏；1969年美国765千伏；1985年苏联1150千伏特高压投运，后降压至500千伏运行。
+- **中国电压等级**：220千伏于1941年投运，330千伏于1972年，500千伏于1981年，**1000千伏于2009年投运**（交流特高压标志性成果）。
+- **直流输电复兴**：交流大电网稳定问题突出后，直流在联网中的优势显现，用于电网与电网之间连接。
+- **现代直流工程**：1954年瑞典本土与哥特兰岛建成世界第一个工业用海底电缆直流工程，100千伏、96公里，采用汞弧阀；1970年扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。
+- **中国直流工程**：第一个直流输电工程连接舟山群岛与浙江定海电网；1989年葛上直流（葛洲坝电厂至上海）±500千伏；近年投运云广直流±800千伏特高压直流工程。
+- **推荐阅读**：主讲人推荐三本书供学生课后阅读，了解电力发展史。
+## 三相交流输电的优势
 - **优点一**：三相系统易于产生旋转磁场，三相电动机容易做驱动。
 - **优点二**：三相系统瞬时功率恒定，不随时间变化。
-- **优点三**：输电线路导线量（金属消耗量）最少。
-- **应用范围**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内高压、超高压、特高压输电大多采用三相交流，联网时才采用直流。
-- **效率比较**：三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小（全截面为一根导线截面乘以3），因此得到广泛应用。
+- **优点三**：输电线路导线金属消耗量最少。
+- **应用范围**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内电力系统大多数高压、超高压、特高压输电采用三相交流，联网时采用直流。
+- **效率比较**：三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小，因此在交流输电领域广泛应用，目前仍采用此方式。
 ## 电力系统的形成
-- **单机供电缺陷**：早期一台发电机向附近负荷供电，发电机出问题负荷即停电，供电可靠性差。
-- **并联提高可靠性**：将多台发电机并联连接，一台出问题时另一台可带重要负荷，可靠性提高。
-- **输电线路参数限制**：导线有电阻和电抗两个重要参数，传输功率时产生电压损耗和功率损耗，阻抗越大、电流越大损耗越大，输电距离不能太长。
-- **升压解决距离问题**：提高电压后传输相同功率时电流减小，有功功率损耗（I²R）和电压降落（IZ）均减小，输电距离变长；交流升压采用变压器，一侧升压、另一侧降压。
+- **单机供电缺陷**：一台发电机向附近负荷供电，发电机出问题负荷即停电，供电可靠性差。
+- **并联提高可靠性**：将多台发电机并联，一台故障时另一台可带重要负荷，可靠性提高。
+- **线路阻抗问题**：导线有电阻和电抗两个重要参数，传输功率时产生电压损耗和功率损耗；阻抗越大、电流越大，损耗越大，输电距离不能太长。
+- **升压解决距离问题**：电压升高后传输相同功率时电流减小，有功功率损耗（I²R）和电压降落（IZ）均减小，输电距离可变长；交流升压采用变压器，一侧升压、另一侧降压。
 - **电力系统雏形**：近距离（几十至几百米）发电机直接相连，远距离升压传输，多台发电机共同供电，形成电力系统雏形。
-- **系统化好处**：发电机数目足够多时可保证供电；可装大机组向大片区域供电，供电范围扩大，带来直接经济效益。
-- **现代电力系统特征**：发电机发电→升压变压器升压→输电线路传输到负荷中心→降压后供给用电设备；输电距离很长时中间装设变电站降压向沿途供电，并可引接部分负荷。
-## 电力系统、电力网与动力系统定义
-- **电力系统定义**：由发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个方面的职能，由发电、输电、配电、用电四个环节组成。
-- **电力网定义**：变压器和输电线路构成的网络，即电力系统去除发电机和用电设备的部分。
-- **动力系统定义**：电力系统加上发电厂动力部分（火电厂的锅炉、汽机、煤炭输送处理系统；水电厂的水轮机、水坝、水库等）。
-- **概念辨析**：行业中最常说的是电力网和电力系统两个概念，动力系统现在很少说；「电网」通常指电力网。
+- **系统化好处**：发电机数目足够多时单台停机不影响供电；可装大机组向大范围供电，供电范围扩大，带来直接经济效益。
+- **远距离输电**：距离很长时（如湖北送电华东、云贵送电两广），输电线路中间可装设变电站降压向当地供电，并可引接部分负荷；输电距离长还出现稳定问题，可装设变电站采取设备调整。
+## 电力系统、电力网与动力系统
+- **电力系统定义**：发电机、变压器、输电线路和用电设备构成的整体，完成电能**生产、输送、分配、消耗**四个环节职能，由发电、输电、配电、用电四个环节组成。
+- **电力网定义**：变压器和输电线路构成的网络，即电力系统去除发电机和用电设备的部分；行业中最常说的是电力网和电力系统两个概念。
+- **动力系统定义**：电力系统加上发电厂动力部分，如火电厂的锅炉、汽机及煤炭输送处理系统，水电厂的水轮机、水坝、水库等。
+- **现代电力系统特征**：发电机发电→升压变压器升压→输电线路传输到负荷中心→降低电压后供用电设备使用。
 ## 电网分类
-- **地方电力网**：向固定地方供给电能的网络，电压等级110千伏及以下（早期定义35千伏及以下），供电半径20~50公里；典型例子为武汉电网（主要供电电压110千伏和35千伏，少数地方出现220千伏）。
-- **区域电力网**：电压等级110、220千伏及少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心；典型例子为华中电网。
-- **超高压远距离输送网络**：电压等级500千伏或1000千伏（东北有330千伏），主要任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统；典型例子为山西晋东南至湖北荆门特高压线路（跨三省、连接华北和华中电网）、葛上直流、三峡至上海输电线路。
-- **电压等级变化**：随着电网发展和电压等级提高，各级电网所用电压等级会发生变化，一般趋向提高。
+- **地方电力网**：向固定地方供给电能的网络，电压等级在110千伏及以下（早期定义为35千伏及以下），供电半径20–50公里。
+- **区域电力网**：电压等级为110、220千伏及少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心的网络。
+- **超高压远距离输送网络**：电压等级500千伏或1000千伏（东北有330千伏），主要任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统。
+- **实例**：武汉电网属地方电力网，主要供电电压110千伏和35千伏，少数220千伏；华中电网属典型区域电网；葛上直流、三峡到上海输电线路属超高压远距离输电网络；晋东南至湖北荆门特高压线路跨三省、连接华北和华中电网，属超高压远距离输送网络。
+- **动态变化**：随着电网发展和电压等级提高，各级电网所用电压等级会发生变化，一般趋向提高。
 ## 变电站分类
-- **按最高电压等级分类**：以站内最高电压等级命名，如华工变电站10千伏变380伏为10千伏变电站；关山变电站最高电压220千伏为220千伏变电站；凤凰山变电站最高电压500千伏为500千伏变电站。
-- **按主要功率流向分类**：大部分功率从高压侧流向低压侧为**降压变电站**；发电厂内大部分功率从低压侧（发电机）升到高压侧为**升压变电站**。
+- **按最高电压等级分类**：以站内最高电压命名，如华工变电站10千伏变380伏为10千伏变电站，关山变电站最高电压220千伏为220千伏变电站，凤凰山变电站最高电压500千伏为500千伏变电站。
+- **按主要功率流向分类**：主要功率从高压侧流向低压侧为**降压变电站**；发电厂内大部分功率从低压侧升到高压侧为**升压变电站**。
 # 课堂互动与答疑
 **学生**：为什么我国电力系统采用交流三相三线制输电，而不是直流或其他方式？
-**教师**：三相交流系统具有三个优势：易于产生旋转磁场，便于三相电动机驱动；瞬时功率恒定，不随时间变化；同等功率和功率因数下输电线路金属消耗量最少。三相三线制传输效率在各类输电方式中最高，金属消耗量最小，因此除室内配电等小功率场合采用单相交流外，其余基本采用三相交流。国内高压、超高压、特高压输电均采用三相交流，仅在电网联网时采用直流方式。
+**教师**：三相三线制在同等功率和功率因数下传输效率最高，且导线金属消耗量最小。三相交流系统具有三个优点：易于产生旋转磁场便于电动机驱动、瞬时功率恒定、导线用量最少。除室内配电等小功率场合用单相外，其余基本采用三相交流；直流仅用于电网间联网。
 # 课后任务与学习建议
 ## 复习重点
-- **电力系统四个环节**：发电、输电、配电、用电的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念。
-- **电力系统、电力网、动力系统定义**：电力系统＝发电机＋变压器＋输电线路＋用电设备，完成电能生产、输送、分配、消耗；电力网＝去除发电机和用电设备后的变压器与输电线路网络；动力系统＝电力系统加上发电厂动力部分（锅炉、汽机、水轮机等）。
-- **电力系统特点引出的基本原理**：电能不能大量储存，决定有功功率和无功功率的动态平衡问题，是电力系统运行调整和设计的基础。
-- **额定电压规定**：规定繁杂，需寻找各额定电压规定之间的基本规律，注意使用条件变化时结论可能失效。
-- **电能质量指标**：掌握国家标准对各电能质量指标规定的范围。
-- **中性点接地方式**：工作接地（中性点接地方式）的不同特点，直接影响后续多个章节内容，学习难度较大。
-- **三相交流输电优势**：三相系统易于产生旋转磁场、瞬时功率恒定、输电线路金属消耗量最少；三相三线制传输效率最高，同等功率和功率因数下金属消耗量最小。
-- **电网分类**：地方电力网（110千伏及以下，早期35千伏及以下，供电半径20~50公里）；区域电力网（110、220千伏及少量500千伏，供电半径超过50公里）；超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，跨省跨地区）。
-- **变电站分类**：按最高电压等级分为10千伏、220千伏、500千伏变电站等；按主要功率流向分为降压变电站（高压侧流向低压侧）和升压变电站（低压侧流向高压侧）。
+- **电力系统基本概念**：掌握电力系统、电力网、动力系统、变电站的定义与区别——电力系统由发电机、变压器、输电线路和用电设备构成，完成电能生产、输送、分配、消耗四个环节；电力网为去除发电机和用电设备后的变压器与输电线路网络；动力系统在电力系统基础上计入发电厂动力部分（火电锅炉汽机、水电水轮机水坝等）。
+- **电力系统特点与要求**：理解电力系统特点及其引起的设计、运行、维护方面的基础理论，以及对电力系统提出的要求；重点掌握电能不能大量储存所决定的有功功率和无功功率动态平衡问题，这是运行调整和设计的基础。
+- **电能质量指标**：掌握国家标准对电能质量指标规定的各种范围，作为第一章重点内容掌握。
+- **额定电压规定**：注意寻找额定电压规定之间的基本规律，该部分规定繁杂，需理清脉络而非死记。
+- **中性点接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地方式）的不同特点；该内容直接影响后续多个章节，学习难度较大。
+- **电网分类**：地方电力网（110千伏及以下，供电半径20–50公里，如武汉电网）；区域电力网（110、220千伏及少量500千伏，供电半径超50公里，如华中电网）；超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，跨省跨地区，如葛上直流、三峡到上海输电线路）。
+- **变电站分类**：按最高电压等级分为10千伏、220千伏、500千伏变电站等；按主要功率流向分为升压变电站（发电厂内）和降压变电站（大部分功率从高压侧流向低压侧）。
+- **三相交流输电优势**：三相三线制传输效率最高，同等功率和功率因数下金属消耗量最小；三相系统易于产生旋转磁场、瞬时功率恒定，除室内配电等小功率供电外均采用三相交流，联网时才采用直流。
 ## 学习建议
-- **补充前修知识**：对电路理论和电机学知识有欠缺的同学，应补充变压器和同步电机的相关知识，本课程对此要求较高。
-- **掌握概念方法**：对基本概念注意其内涵和外延，并适当记忆；思考时从电力系统的特点和要求出发，从最基础原理推导，不要死记结论。
-- **寻找规律与比较**：注意寻找额定电压规定之间的基本规律；比较不同中性点接地方式之间的特点。
-- **课后阅读电力发展史**：作为电气专业学生应了解电力发展的基本历史，主讲人推荐三本书供课后阅读。
-- **结合实例理解电网分类**：通过武汉电网（地方电力网）、华中电网（区域电网）、晋东南至荆门特高压线路及三峡至上海输电线路（超高压远距离输送网络）等实例对比，理解电网分类标准。</t>
+- **补充前修知识**：对电路理论和电机学（特别是变压器和同步电机）有欠缺的同学，应自行补充相关内容，本课程对这两部分知识要求较高。
+- **掌握概念方法**：学习基本概念时注意其内涵和外延，并适当结合实际；思考时从电力系统的特点和要求出发，从最基础原理推导，不要只记结论——使用条件变化时结论可能失效。
+- **比较归纳规律**：注意寻找额定电压规定之间的基本规律，比较各种不同中性点接地方式之间的特点，学完章节后再仔细体会辅导性内容。
+- **课后拓展阅读**：作为电气专业学生应了解电力发展基本史，主讲人推荐三本书供课后阅读，了解交直流输电发展历程及交流输电占主导的原因。</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>82.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11163/5739</t>
+          <t>11163/5783</t>
         </is>
       </c>
     </row>
@@ -4863,69 +4845,58 @@
       <c r="C14" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本期视频围绕调和级数发散性的证明展开，属于数学分析领域，核心问题是调和级数∑1/n为何发散以及不同证明方法的优劣。整体逻辑框架按「定义 → 方法评点 → 结论倾向」推进：先介绍级数收敛与发散的定义，再逐一评论网友在Stack Exchange上给出的分组估计、积分估计、差分法等证明，并补充柯西凝聚判别法作为延伸。皮卡的整体立场是：调和级数发散这一结论本身无争议，但部分证明方法（如利用指数不等式放缩、Stolz定理）属于「先射箭后画靶」，技巧性强却故弄玄虚，妨碍理解；他更推崇思路自然、与分组求和本质一致的方法。
+本期视频围绕调和级数∑1/n的收敛与发散性展开，核心问题是：如何证明调和级数发散，以及不同证明方法的优劣。视频以评论Stack Exchange上网友的证明为主线，按“定义级数收敛与发散 → 逐一评论网友证明 → 补充与批评”的逻辑推进。皮卡先给出收敛与发散的直观定义，随后评论第一个网友的分组估计证明（每组和大于1/2），并指出其与柯西凝聚判别法思路完全一致；接着评论第二个网友证明hn &gt; log(n+1)的方法，认为其技巧性强但可能故弄玄虚，并介绍积分估计法与差分法作为更自然的替代。整体立场是：调和级数确实发散，但部分证明方法（如使用Stolz定理的差分法）因事先知道结果而显得不自然，属于“先射箭后画靶”，而分组求和与积分估计等思路更本质、更易理解。
 # 核心概念
-## 级数收敛与发散的定义
-- **收敛**：对正向级数，若存在固定实数 `a`（上界），使得任意正整数 `n` 对应的部分和 `s_n` 都满足 `s_n &lt; a`，则称级数收敛。
-- **发散**：若能证明 `s_n` 大于某个单向递增且永无止境的 `b_n`——即无论给出多大的数 `b`，总可通过增大 `n` 使 `b_n` 超过 `b`——则级数发散。
-- 皮卡指出，这是对收敛与发散判断的简化处理，只需考虑部分和是否有上界。
-## 分组求和法（第一个网友的证明）
-- 将调和级数分组：`1` 单独一组，`1/2 + 1/3` 一组，`1/4 + 1/5 + 1/6 + 1/7` 一组，`1/8` 至 `1/15` 一组，依此类推。
-- 每组和均大于 `1/2`：如 `1/2 + 1/3 &gt; 1/4 + 1/4 = 1/2`，`1/4` 至 `1/7` 四项均大于 `1/8`，四项之和 `&gt; 4 × 1/8 = 1/2`。
-- 由于级数包含任意多组，每组和都大于 `1/2`，任意多个 `1/2` 相加无上界，故调和级数发散。
-- 皮卡评价：这是微积分前几堂课常见的方法，其核心思路是发现具有良好性质的组，将求和问题转化为数组的个数。
+## 调和级数与收敛发散定义
+- **级数收敛**：对正项级数，若存在固定实数 a，使所有部分和 `sₙ` 均小于 a（无论 n 取多大），则称其收敛；反之若部分和可超过任意给定数，则发散。
+- **调和级数**：`∑1/n`，其部分和记为 `Hₙ = 1 + 1/2 + … + 1/n`，英文为 harmonic，是经典的发散级数。
+- 皮卡指出，微积分虽为清朝初年（康熙治鳌拜时期）提出的数学分支，但因数学传播困难，多数人对调和级数收敛性并不清楚，互联网上（如民科吧）曾有人主张调和级数收敛并引发论战。
+## 分组求和证明
+- 第一个网友的证明思路：将调和级数分组，`1` 单独一组，`1/2 + 1/3` 一组，`1/4 + 1/5 + 1/6 + 1/7` 一组，`1/8` 至 `1/15` 一组，依此类推。
+- 关键推演：每组内各项均大于该组项数对应的 `1/2^k`，故每组和均大于 `1/2`；级数包含任意多组，每组贡献超过 `1/2`，因此部分和无上界，级数发散。
+- 皮卡评价：该证明是微积分前几堂课常见内容，其分组取上下界估计的思路与**柯西凝聚判别法**的证明完全一致。
 ## 柯西凝聚判别法
-- 皮卡指出，**柯西凝聚判别法**的证明过程与分组求和法完全一致：分组、每组的估计、对部分和的整体估计。
-- 对非负不增序列，其收敛发散性质等价于 `∑ 2^k · a_{2^k}` 的收敛发散性质。
-- 应用于调和级数：`∑ 1/n` 的收敛性等价于 `∑ 2^k · (1/2^k) = ∑ 1`，无穷个 1 相加显然无上界，故发散。
-- 皮卡推测柯西当年正是将分组求和的想法推广到任意非负不增序列的和上。
-## 高斯求和与分组思想
-- 高斯小时候计算 `1 + 2 + 3 + … + 100`，采用 `1 + 100 = 101`、`2 + 99 = 101` 的分组方式，只需数有多少个 `101`。
-- 皮卡指出，分组求和或分组估计的思路在数学中相当普遍：若能在求和中发现一个组，其满足估计要求、和恒定或有某种模式，问题就变得简单。
-- 一旦发现这样的组，求和问题就转化为对每组做估计或求和，最终只需数有多少个组。
-## 对数下界证明（第二个网友的证明）
-- 该证明的目标是证明 `h_n &gt; log(n+1)`，其中 `h_n = 1 + 1/2 + … + 1/n` 是调和级数的部分和。
-- 由于 `log(n+1)` 无上界，故 `h_n` 也无上界，级数发散。
-- 皮卡指出，`log` 即自然对数 `ln`，美国写法为 `log`，欧洲写法为 `ln`，中国沿袭欧洲写法。
-- 皮卡认为此证明技巧性强，第一次看可能惊为天人，但充满巧合，可能是作者知道结果后反推凑出来的。
+- 定义：对非负不增序列，级数 `∑aₙ` 的收敛发散性等价于 `∑2ᵏ·a₂ᵏ` 的收敛发散性。
+- 推演：将原级数按 `2ᵏ` 个元素分组，每组做上下界估计，转化为对加速后序列的求和判断；对调和级数，`∑2ᵏ·(1/2ᵏ) = ∑1`，无穷个 1 相加无上界，故发散。
+- 适用条件：针对增长缓慢、不易直接判断收敛性的序列，凝聚判别法可产生本质性简化；皮卡推测柯西当年正是从分组求和推广到一般非负不增序列。
+- 皮卡补充：分组求和思想在**高斯**幼年计算 `1+2+…+100` 时也有体现——首尾配对恒为 101，只需数配对数；发现具有良好性质的分组后，求和问题转化为数有多少组。
+## 对数下界证明
+- 第二个网友的证明目标：证明 `Hₙ &gt; log(n+1)`，因 `log(n+1)` 无上界，故 `Hₙ` 也无上界，级数发散。
+- 关键步骤：对 `e^(Hₙ)` 做放缩，利用 `e^(1/k) &gt; 1 + 1/k`，将指数和转化为连乘积 `∏(1 + 1/k)`，相邻项相消后恰为 `n+1`，取对数即得 `Hₙ &gt; log(n+1)`。
+- 皮卡评价：该证明技巧性强、首次看可能惊为天人，但本质是**后期凑出来的**——先知道结果再反推；与对数差分不等式两边求和、相邻项相消的思路完全等价，属于故弄玄虚、变魔术式的写法，妨碍理解却让人感觉 magic。
 ## 积分估计法
-- 用积分曲线面积近似 `h_n`：部分和从几何上看是矩形面积（高为 `1/n`，底为 1），矩形始终大于下方曲边梯形面积。
-- 因此 `h_n` 始终大于积分 `∫ 1/x dx = log x` 的定积分值，从而得到 `h_n &gt; log(n+1)` 的下界。
-- 皮卡评价：这是正规的流派，通过积分放缩判断级数收敛性，比技巧性强的证明更自然。
-## 差分法（Stolz 定理）
-- 该流派试图证明 `h_n` 与 `log n` 是同一增长级别，因 `log n` 无上界，故 `h_n` 也无上界。
-- 使用 **Stolz 定理**（中文称施托尔茨定理）：对分子分母均为无穷大的 `a_n / b_n`，可考虑其差分 `(a_{n+1} - a_n) / (b_{n+1} - b_n)` 的极限。
-- 对调和数，分子差分是最后一项 `1/(n+1)`，分母差分是 `log(1 + 1/n)`，两者求极限为 1，故 `h_n / log n → 1`。
-- 皮卡批评此证明不自然：作者事先知道 `h_n` 满足 `log(n+1) &gt; h_n &gt; log n` 的不等式，才选择除以 `log n`；若不知道结果，没有理由不选 `√n` 或 `log log n` 的平方。
+- 思路：用积分曲线面积近似部分和 `Hₙ`；调和级数各项可视为高为 `1/n`、底为 1 的矩形面积，矩形面积始终大于下方曲边梯形面积。
+- 推演：`∫₁ⁿ⁺¹ (1/x) dx = log(n+1)`，故 `Hₙ &gt; log(n+1)`，与第二个网友结论一致但更自然。
+- 皮卡评价：这是正规流派的做法，属于「和的积分估计」，内容较多，是证明调和级数发散的更自然路径。
+## Stolz 定理证明
+- 思路：证明 `Hₙ` 与 `log n` 同增长级别，因 `log n` 无上界故 `Hₙ` 发散；使用 **Stolz 定理**（中文常称施托尔茨定理）比较 `Hₙ/log n` 的极限。
+- 关键步骤：分子差分 `Hₙ₊₁ - Hₙ = 1/(n+1)`，分母差分 `log(n+1) - log n = log(1 + 1/n)`，两者比值极限为 1，故 `Hₙ/log n → 1`。
+- 皮卡评价：该证明**不自然**，属于「先射箭后画靶」——因为事先知道 `Hₙ` 满足 `log(n+1) &gt; Hₙ &gt; log n` 这一基本估计，才选择除以 `log n`；若不知结果，没有理由不猜 `log log n` 或 `√n`。
 # 核心结论
 ## 核心结论
-- **调和级数发散**：级数 ∑1/n 的前 n 项和 sn 无上界，即对任意给定实数 a，总可通过增大 n 使 sn 超过 a，故发散。
-- **收敛定义**：对任意正整数 n，若所有 sn 都小于某个固定实数 a（上界），则级数收敛；反之若 sn 大于某个单调递增且无界的 bn，则发散。
-- **第一个网友的分组证明**：将调和级数分组为 {1}、{1/2, 1/3}、{1/4, 1/5, 1/6, 1/7}、{1/8, …, 1/15} 等，每组和均大于 1/2，因组数无限多，总和无上界，故发散。
-- **柯西凝聚判别法**：对非负不增序列，其级数收敛发散性质等价于 ∑2^k·a(2^k)；证明思路与分组求和完全一致，只需数有多少组（组数无界）即可。
-- **第二个网友的证明**：证明 hn &gt; log(n+1)，因 log(n+1) 无上界，故 hn 发散；该证明技巧性强，但皮卡认为作者是事先知道结果后反推凑出来的，属于「故弄玄虚」。
-- **积分估计法**：hn 从几何上可看作矩形面积之和，始终大于曲线 f(x)=1/x 下方的曲边梯形面积，即大于 ∫₁ⁿ⁺¹(1/x)dx = log(n+1)，从而证明发散。
-- **差分法（Stolz 定理）**：比较 hn 与 log n 的差分，分子差分为 1/(n+1)，分母差分为 log(1+1/n)，两者比值极限为 1，故 hn 与 log n 同增长级别，log n 无上界所以 hn 发散。
-- **皮卡对差分法的批评**：该方法不自然，属于「先射靶后画箭」——作者事先知道 hn 满足 log n 的估计不等式才选择除以 log n，若不知道结果不可能凭空猜出 log n（而非 log log n 的平方或 √n）。
+- **调和级数∑1/n是发散的**：皮卡在评论中确认这一结论，并指出对学过高等数学的大学生而言是简单问题。
+- **第一个网友的证明（分组估计法）**：将调和级数各项分组，第一组为1，第二组为1/2+1/3，第三组为1/4+1/5+1/6+1/7，依此类推；每组和均大于1/2，由于可构造任意多组，部分和无上界，故级数发散。
+- **柯西凝聚判别法**：皮卡指出其证明过程与分组求和想法完全一致——对非负不增序列，∑a_n的收敛发散性等价于∑2^k·a_{2^k}的收敛发散性；应用于调和级数时，等价于∑2^k·(1/2^k)=∑1，无穷个1相加无上界，故发散。
+- **第二个网友的证明（hn &gt; log(n+1)）**：证明调和数部分和hn大于log(n+1)，而log(n+1)无上界，故hn发散；皮卡认为此证明技巧性强，但可能是先知道结果再反推凑出来的。
+- **积分估计法**：用积分曲线面积近似hn，矩形面积始终大于下方曲边梯形面积，可算出定积分得log x，从而给出hn &gt; log(n+1)的下界；皮卡认为这是更正规的流派。
+- **差分法（Stolz定理）**：比较hn与log n的差分，分子差分为1/(n+1)，分母差分为log(1+1/n)，两者求极限为1，故hn与log n同增长级别，log n无上界所以hn发散；皮卡批评此法不自然，属于"先射箭后画靶"——事先知道hn满足log n+1 &gt; hn &gt; log n的不等式才选择除以log n。
 ## 易混点与适用边界
-- **收敛与发散的判断标准**：收敛要求所有 sn 都被某个固定实数 a 控制（上界存在）；发散则是 sn 的下界永无止境，两者互为否定，判断时只需验证其一。
-- **柯西凝聚判别法的适用条件**：仅适用于**非负且不增**的序列；对增长很慢、不易直接判断收敛性的级数尤其有效，可将原级数转化为加速后的序列 ∑2^k·a(2^k) 来判断。
-- **分组求和的通用思路**：若能在求和中发现一组具有良好性质的分组（满足估计要求、和恒定或有某种模式），问题可简化为「数有多少组」；高斯求 1+2+…+100 用的也是同一思路。
-- **积分估计的几何边界**：hn 的矩形面积**始终大于**曲边梯形面积（即大于积分值），这是该放缩方向成立的前提；若方向反了则不能得出同样结论。
-- **Stolz 定理的适用前提**：适用于分子分母均为无穷大的形如 an/bn 的极限问题，通过比较差分 an+1−an 与 bn+1−bn 的极限来间接求原极限；但皮卡指出，选择哪个函数作分母需要事先知道答案，否则无从下手。
-- **常见误区**：皮卡认为第二个网友的证明「纯粹就是装」，本质与积分估计法完全是一回事，只是通过取对数、连乘积放缩等技巧包装成看似神奇的形式，反而妨碍理解。
-- **ln 与 log 的记法差异**：ln 是欧洲记法（经苏联传入中国），log 是美国记法，两者在原文中指同一函数（自然对数），并非不同概念。
+- **收敛与发散的定义**：正向级数收敛需所有部分和sn都小于某个固定实数a（上界）；发散则需证明sn大于某个单向递增且永无止境的bn。
+- **柯西凝聚判别法的适用条件**：仅适用于非负不增序列；对增长缓慢、不易直接判断收敛性的级数有本质帮助。
+- **分组求和的通用思路**：若能在求和中发现具有良好性质的组（满足估计要求、和恒定或有某种模式），问题可简化为数有多少组；高斯求1+2+…+100（1+100=101，数50个101）与凝聚判别法同属此思路。
+- **hn与log n的关系**：调和级数基本估计为log(n+1) &gt; hn &gt; log n，两边除以log n取极限为1；皮卡认为不知道此结果时不可能凭空猜出除以log n，故Stolz定理证法不自然。
+- **常见误区**：皮卡批评第二个网友的证明"故弄玄虚""装逼"，本质是变魔术式的障眼法——用指数函数和连乘积放缩掩盖了与对数差分不等式等价的实质；e^x &gt; 1+x这一不等式本身需要微积分基础，而微积分建立在极限之上。
 ## 待澄清问题
-- **后续评论计划未定**：皮卡表示「后面还有很多方法」，但是否推出下一期评论视频取决于本期反响；若反响不错，将再找帖子或网友投稿的解题思路进行评论。
-- **dyadic 分解未展开**：皮卡提到第一个证明背后还有「dyadic 分解」的思路，但因视频时长限制未详细讲解，留待后续。</t>
+- **dialectic分解**：皮卡提及第一个证明背后还有dialectic分解的思路，但表示"一时半会也讲不清楚"，留待后续。
+- **后续评论计划**：皮卡表示后面还有很多证明方法，若本期反响不错将出下一期，再找帖子或网友投稿的解题思路进行评论。</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>33.9</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7465/3567</t>
+          <t>7465/3236</t>
         </is>
       </c>
     </row>
@@ -4988,93 +4959,68 @@
       <c r="C15" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本期内容聚焦于GitHub这一全球开源资源平台，围绕“如何高效利用GitHub获取资源并解决使用中的常见问题”这一核心议题展开。整体逻辑框架分为三块并列推进：首先介绍GitHub上的实用热门项目，涵盖工作性价比评估、表情包合集、健康指南、证件照制作、健身指导、教材下载、声音克隆及AI学习资源库等；其次针对国内用户访问GitHub时遇到的网络不通、全英文界面、搜索功能不好用等痛点，逐一给出解决方案，包括使用加速软件、镜像站、VPN、翻译插件及AI辅助搜索；最后讲解GitHub项目页面的核心功能模块（如watch、fork、star、release、read me）与判断项目活跃度的方法。整体立场倾向于将GitHub定位为“巨大的宝藏资源库”，并明确推荐使用AI工具（如ChatGPT）替代原生搜索以提升检索效率，同时强调加速软件与魔法（VPN）是流畅访问的优选方案。
+本期分享围绕GitHub这一开源资源平台展开，核心问题是：如何高效发现实用项目，并解决国内用户访问慢、英文界面、原生搜索不好用等使用障碍。整体逻辑框架分两条线索推进：先以项目介绍切入，依次展示工作性价比评估、表情包博物馆、健康指南、一键证件照、自重健身、教材合集、声音克隆（ChatBox TTS）、AI学习资源库等热门项目；再转向使用技巧，按“访问加速→页面汉化→搜索优化→项目主页解读”的顺序，逐一给出解决方案。整体立场倾向明确：GitHub是人人可用的资源宝库，访问与搜索问题均有可行替代方案，其中AI工具搜索与加速软件被重点推荐。
 # 核心概念
 ## GitHub 资源库定位
-- **GitHub** 被定位为「巨大的宝藏资源库」，几乎想找的资源、教程、工具都能找到，而非仅限程序员使用的平台。
-- 正经资源包括名校公开课（麻省理工、斯坦福）、大厂面试题与经验（字节、阿里、腾讯）、大公司最新开源大模型、AI 副业教程、AI 学习资料等。
-- 不正经资源包括国内近年全网爆火的表情包大合集、活到 150 岁养生指南、国内 996 最严重的大厂黑名单等。
-## 工作性价比评估项目
-- 项目名为「b班值不值得上」，用于评估工作性价比高低，判断「牛马当得值不值」。
-- 输入参数包括年薪、工作地区、年假、通勤时长、学历、工作年限，以及领导同事是否「SB」等因素。
-- 系统综合上述因素后给出工作性价比分数和评级；发言者2测试程序员工作，评估结果为「性价比还不错，优质牛马」。
-## 表情包博物馆项目
-- 收录国内过去这些年全网爆火的表情包大合集，整理较全，包括甄嬛传、罗翔、特朗普、马保国等主题。
-- 用途为斗图场景，发言者2称「如果你斗图用这个，你可以把对方按在地上摩擦」。
-## 健康指南项目
-- 名为「教你健康的活到150岁指南」，分享经过科学证实的健康知识。
-- 具体内容包括间歇性进食对身体有好处，会促进胆汁代谢、炎症自愈；吃天然发酵类食品可改善肠道菌群生态。
-- 发言者2评点：不指望活到 150 岁，只希望教程能让自己活到领养老金那天。
-## 一键做证件照项目
-- 只需上传一张大头照，即可一键抠图换背景，生成不同标准的证件照和各种规格的打印模板。
-## 健身教练项目
-- 提供自重、哑铃、弹力带、长凳等健身方式，选择练习的肌肉群后给出参考动画，可跟着做。
-- 发言者2评点：适合请不起真人教练的人，称为「丐版健身教练」。
-## 教材合集项目
-- 收集国内所有小学、初中、高中及一部分大学的 PDF 教材，全部免费使用。
-- 发言者2评点：当年撕掉发誓不再读的课本在这里都能找回来。
-## 声音克隆模型 ChatBox TTS
-- 属于零样本语音克隆模型，特点是情感控制非常到位，克隆的声音像真人说话一样。
-- 使用方式：打开项目网页，上传一段自己的音频，合成一段英文台词即可听效果。
-## AI 学习资源库
-- 涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术。
-- 作者将所有教程整理成一份 500 多页的 PDF 文档，内含大量示意图帮助理解，实用性很强。
-## Awesome AI Apps 项目
-- 收录大模型最新的 Agent 应用，包括医学影像数据分析 Agent、AI 投资 Agent、竞争对手情报分析 Agent 等。
-- 用途：跟进 AI 应用落地最新案例或寻找创业点子。
-## GitHub 访问加速方法
-- **方法一**：使用 `watch tool Kit` 加速软件，进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选 GitHub 加速即可流畅访问。
-- **方法二**：使用 GitHub 镜像站（如 `gh proxy`），浏览器点开即可直接访问 GitHub，默认是镜像的项目地址，搜索其他项目无问题。
-- **方法三**：使用魔法（VPN），需先注册 GitHub，注册简单，用国内 QQ 邮箱即可。
-- 发言者2评点：大多数人用 `watch tool Kit` 更流畅，镜像站速度和稳定性较差，个人最推荐魔法方式。
-## GitHub 页面汉化
-- 给浏览器安装翻译插件即可解决全英文界面问题，谷歌浏览器推荐 `谷歌translate` 或 `沉浸式翻译`。
-- 安装方式：点开三个点 → 拓展程序 → 管理拓展程序 → 搜索插件名字安装。
-- 动手能力强的还可安装汉化插件，它本身也是个 GitHub 项目。
-## GitHub 搜索方法
-- **原生搜索**按搜索词精准匹配排序，默认按匹配度排序，但更常用按 star 数排序；star 数代表项目的「江湖地位」，越多说明越受欢迎。
-- 原生搜索对国人不太好用，因精准匹配导致同义词搜出不同结果，如搜 `screen record` 和 `screen recording` 按星标排序结果不一样。
-- **推荐用 AI 搜索**：在 ChatGPT 中用中文提出需求（如「在 GitHub 上帮我找好用的录屏软件」），AI 可搜齐热门工具并总结成表格，解决英文不好、搜索不准确不全面的问题。
-## GitHub 项目页面结构
-- 一个项目本质上就是一个文件夹，项目名字下面是子文件夹或文件。
-- 项目上方是「一键三连」区域：`watch` 是关注项目，`fork` 是复制项目到自己的账号，`star` 相当于收藏和点赞。
-- 右侧 `About` 是项目简介，一句话介绍项目是干啥的；下方是项目遵守的开源协议。
-- `release` 是软件的安装包，点开可看到最新版本安装包，下载安装即可使用。
-- 像样一点的项目一般都有 `read me` 文件，即项目说明书，默认在项目最下面展开显示，可了解项目用途、安装使用方法，是了解项目必看的内容。
-- 每个文件最近的 `commit` 日期可理解为最近更新时间，若更新日期是好几年前，大概率是没人维护的僵尸项目。
-## 热门项目追踪
-- 点开左侧 `Explore`，在 `Trending` 里可看到全站当天、本周、本月最热门的项目，最新热门项目看这里。
-- 另一种更推荐的方式是借助 ChatGPT 等工具，如让 ChatGPT 找 GitHub daily，可及时分享各种最新最热门的项目。
+- **GitHub** 不只是代码托管平台，更是「每个人都可以用的巨大的宝藏资源库」，几乎想找的资源、教程、工具都能找到。
+- 正经资源包括名校公开课（麻省理工、斯坦福）、大厂面试题与经验（字节、阿里、腾讯）、大公司最新开源大模型、AI 搞副业教程、AI 学习资料等。
+- 不正经资源包括国内全网爆火的表情包大合集、活到 150 岁养生指南、996 最严重大厂黑名单等。
+## 实用热门项目
+- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事是否 SB 等因素，综合给出工作性价比分数和评级；主讲人测试程序员工作，评估结果为「性价比还不错，优质牛马」。
+- **表情包博物馆项目**：收录国内过去几年全网爆火的表情包大合集，包括甄嬛传、罗翔、特朗普、马保国等主题，可用于斗图。
+- **健康指南项目**：分享经科学验证的健康知识，如间歇性进食可促进胆汁代谢、炎症自愈，吃天然发酵类食品可改善肠道菌群生态。
+- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准的证件照和各种规格的打印模板。
+- **自重健身项目**：选择要练习的肌肉群（如腹肌），提供用身体自重练习的参考动画，适合请不起真人教练的用户。
+- **教材合集项目**：收集国内所有小学、初中、高中及部分大学的 PDF 教材，全部免费。
+- **声音克隆模型 ChatBox TTS**：零样本语音克隆，情感控制到位，克隆声音像真人说话；上传一段音频即可合成指定英文台词。
+- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
+- **awesome AI Apps 项目**：收录大模型最新的 agent 应用，如医学影像数据分析 agent、AI 投资 agent、竞争对手情报分析 agent，适合跟进 AI 应用落地案例或找创业点子。
+## GitHub 访问与加速
+- **watch tool Kit 加速软件**：进入网站选择适合电脑的版本下载安装，打开后找到网络加速并勾选「github 加速」，即可流畅访问 GitHub；主讲人认为对大多数人这是更流畅的选择。
+- **镜像站**：如 `gh proxy`，浏览器点开即可直接上 GitHub，默认是镜像的项目地址，也可搜索其他项目；但速度与稳定性比加速软件差。
+- **魔法（VPN）**：主讲人个人最推荐的方法，但未展开具体操作。
+- **注册**：GitHub 注册很简单，用国内 QQ 邮箱即可。
+## 页面汉化与搜索
+- **翻译插件**：谷歌浏览器推荐安装 `谷歌 translate` 或 `沉浸式翻译` 插件，装好后可直接把网页翻译成中文，翻译效果基本够用；安装路径为「三个点 → 拓展程序 → 管理拓展程序 → 搜索插件名字安装」。
+- **原生搜索局限**：GitHub 原生搜索按搜索词精准匹配排序，如搜 `screen record` 和 `screen recording` 按星标排序结果不一样，对国人不好用。
+- **AI 搜索推荐**：在 ChatGPT 中用中文提出需求（如「在 github 上帮我找好用的录屏软件」），AI 可搜齐热门工具并总结成表格，比原生搜索更全面准确。
+## 项目主页要素
+- **项目本质**：GitHub 上的一个项目本质上就是一个文件夹，项目名字下面是子文件夹或文件。
+- **一键三连**：`watch` 是关注项目，`fork` 是复制项目到自己的账号，`star` 相当于收藏和点赞；star 数代表项目江湖地位，越多说明越受欢迎。
+- **about 与开源协议**：右侧 `about` 是项目简介，一句话介绍项目用途；下方是项目遵守的开源协议。
+- **release**：软件的安装包所在位置，点开可看到最新版本安装包并下载安装。
+- **read me 文件**：项目的说明书，默认在项目最下面展开显示，可了解项目用途、安装使用方法，是了解项目必看的内容。
+- **commit 日期**：每个文件最近的 commit 日期即最近更新时间；若更新日期是好几年前，大概率是没人维护的僵尸项目。
+- **explore / trending**：左侧 `explore` 的 `trending` 中可看到全站当天、本周、本月最热门的项目；也可让 ChatGPT 帮忙找 GitHub daily，及时分享最新热门项目。
 # 核心结论
 ## 核心结论
-- **GitHub 是通用资源库**：不只是代码托管平台，可找到名校公开课（麻省理工、斯坦福）、大厂面试题（字节、阿里、腾讯）、开源大模型、AI 学习资料等正经资源，也有表情包合集、养生指南、大厂黑名单等非正经内容。
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等，综合给出性价比分数和评级；发言者2实测程序员工作获评「性价比还不错，优质牛马」。
-- **表情包博物馆项目**：收录国内过去多年全网爆火的表情包，含甄嬛传、罗翔、特朗普、马保国等主题。
-- **健康指南项目**：分享经科学研究的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，天然发酵类食品改善肠道菌群生态。
-- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照和打印模板。
-- **健身教练项目**：提供自重、哑铃、弹力带等健身动画，可选择肌肉群（如腹肌）获得参考动画。
-- **教材合集项目**：收集国内所有小学、初中、高中及部分大学 PDF 教材，全部免费。
-- **ChatBox TTS 声音克隆模型**：零样本语音克隆，情感控制到位，克隆声音接近真人。
-- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents 等最新 AI 技术，整理成 500 多页 PDF 文档，含大量示意图。
-- **awesome AI Apps 项目**：收录大模型最新 agent 应用，如医学影像数据分析、AI 投资、竞争对手情报分析等，可用于跟进 AI 落地案例或找创业点子。
-- **GitHub 访问三种解法**：① watch tool Kit 加速软件（进入网站选版本下载安装，打开后勾选 GitHub 加速）；② 镜像站（如 gh proxy，浏览器直接访问，但速度与稳定性较差）；③ 魔法/VPN（个人最推荐，需注册 GitHub，国内 QQ 邮箱即可）。
-- **界面汉化方案**：谷歌浏览器推荐谷歌 translate 或沉浸式翻译插件；动手能力强的可安装汉化插件。
-- **原生搜索有局限**：按关键词精准匹配，如搜 screen record 与 screen recording 按星标排序结果不同；推荐用 AI 搜索（如 ChatGPT 输入中文需求），可汇总热门工具并整理成表格。
-- **项目页面功能**：watch 为关注、fork 为复制项目、star 为收藏点赞；About 是项目简介，release 是安装包，read me 是项目说明书（默认在项目最下方展开显示）。
-- **判断项目是否维护**：查看文件最近 commit 日期（即最近更新时间），若更新日期在多年前，大概率是无人维护的僵尸项目。
-- **找热门项目渠道**：Explore → Trending 可看全站当天、本周、本月最热门项目；也可让 ChatGPT 找 GitHub daily 获取最新热门项目。
+- **GitHub是综合性资源库**：可找到名校公开课（麻省理工、斯坦福）、大厂面试题（字节、阿里、腾讯）、开源大模型、AI学习资料及表情包合集等各类资源。
+- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限等参数，综合评估后给出工作性价比分数和评级；主讲人测试程序员岗位结果为「性价比还不错，优质牛马」。
+- **表情包博物馆项目**：收录国内过去数年全网爆火表情包合集，包括甄嬛传、罗翔、特朗普、马保国等主题。
+- **健康指南项目（活到150岁）**：分享经科学验证的健康知识，如间歇性进食可促进胆汁代谢、炎症自愈，吃天然发酵类食品可改善肠道菌群生态。
+- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照及各种规格打印模板。
+- **自重健身项目**：选择目标肌肉群（如腹肌）后提供三个自重练习参考动画，可替代真人教练。
+- **教材合集项目**：收集国内所有小学、初中、高中及部分大学PDF教材，全部免费使用。
+- **声音克隆模型ChatBox TTS**：零样本语音克隆，情感控制到位，克隆声音接近真人说话效果。
+- **AI学习资源库**：涵盖大语言模型、RAG、AI Agents等最新AI技术，作者整理成500多页PDF文档并配有大量示意图。
+- **awesome AI Apps项目**：收录大模型最新agent应用，包括医学影像数据分析、AI投资、竞争对手情报分析等agent，可用于跟进AI应用落地案例或寻找创业点子。
 ## 易混点与适用边界
-- **三种访问方式适用性**：watch tool Kit 加速软件对大多数人更流畅；镜像站速度与稳定性较差；魔法（VPN）为个人最推荐，但需自行注册 GitHub。
-- **原生搜索 vs AI 搜索**：原生搜索按精准匹配，同一意思不同写法（screen record / screen recording）结果不同，易漏；AI 搜索（ChatGPT）可弥补英文不好、搜索不准确不全面的问题。
-- **项目更新状态判断**：commit 日期代表最近更新时间，多年前未更新大概率是僵尸项目；最新热门项目应看 Explore → Trending 或 ChatGPT 推荐的 GitHub daily。</t>
+- **GitHub访问方式对比**：watch tool Kit加速软件需下载安装并勾选网络加速，是更流畅的选择；镜像站（如gh proxy）可直接打开但速度和稳定性较差；魔法（VPN）为主讲人最推荐的方式。
+- **GitHub注册**：使用国内QQ邮箱即可完成注册。
+- **英文页面处理**：谷歌浏览器可安装谷歌translate或沉浸式翻译插件，将网页翻译成中文，翻译效果基本够用；动手能力强的可另装汉化插件。
+- **GitHub原生搜索的局限**：按搜索词精准匹配排序，如搜「screen record」和「screen recording」按星标排序结果不同；推荐改用ChatGPT等AI工具用中文搜索，结果更全面并自动汇总成表格。
+- **项目主页功能区分**：watch是关注项目，fork是复制项目到自己的账号，star相当于收藏和点赞；star数代表项目受欢迎程度（江湖地位）。
+- **项目活跃度判断**：每个文件显示最近commit（更新）日期，若更新日期为好几年前，大概率是无人维护的僵尸项目。
+- **热门项目查看**：通过explore的trending可查看全站当天、本周、本月最热门项目；也可让ChatGPT等AI工具帮忙找GitHub daily分享最新热门项目。
+- **read me文件作用**：是项目说明书，默认在项目最下方展开显示，是了解项目用途、安装使用方法必看的内容。</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>43.9</v>
+        <v>36.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4014/4310</t>
+          <t>4014/3498</t>
         </is>
       </c>
     </row>
@@ -5445,68 +5391,64 @@
       <c r="C16" t="inlineStr">
         <is>
           <t># 访谈概述
-本次访谈由主持人（发言者1）与《明朝那些事》作者当年明月（发言者2）及嘉宾马先生（发言者3）等围绕日本文化精神与明朝历史展开。访谈从热播日剧《大奥》切入，讨论日本文化的极端精神、忠诚文化与中国的差异，随后转入《明朝那些事》的创作与明朝历史解读，覆盖日本文化精神、明朝历史特点、皇帝趣事与审美差异等议题。受访者核心观点包括：日本文化具有极端精神，做事做到尽头，战后用30年成为世界第二经济强国（绝对量）是必然；中国讲中庸，日本坚持原则，终身雇佣制下员工积极性仍高；历史经验教训难以直接套用，引用「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」。访谈看点在于当年明月指出正德皇帝被写坏是因嘉靖非其亲生子、实录有偏颇，以及明末市民生活轻松、江浙工商业兴起的细节。
+本期《锵锵三人行》围绕日本历史剧《大奥》与《明朝那些事儿》展开，探讨中日文化差异及明朝历史特点。受访者包括《明朝那些事儿》作者当年明月（发言者2）与嘉宾马先生（发言者3），由主持人（发言者1）引导对话。访谈主线分两部分：先由《大奥》切入日本文化，覆盖大奥含义、幕府政治、极端精神、忠诚文化、终身雇佣制及战后经济崛起等议题；后转向明史，讨论明史研究难点、朱元璋评价、明朝兴亡经验教训、明末市民生活、明式家具及正德皇帝评价等。受访者核心观点包括：日本文化讲究极端精神，所有事情做到尽头，与中国中庸文化形成对比；明史资料最多但一个事件可能有7个不同说法，如同罗生门；历史经验教训的经典论断——我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。原文关键锚点包括《大奥》三部曲、1644年北京瘟疫（疙瘩瘟）、明朝276年国祚。访谈看点在于当年明月以史料为依据提出正德皇帝被写坏的观点，指出明武宗实录由嘉靖指派杨廷和等人编修，存在偏颇；以及马先生亲述参观日本豆腐厂时工人等到夜里12点整才开始工作的细节，体现日本人的一丝不苟。
 # 访谈详细记录
-## 日本文化精神与《大奥》
-- **《大奥》热播与定位**：发言者1提到《大奥》刚播完并引起很大反响；发言者3认为它是《大长今》以后最有影响的外国电视剧，发言者2表示认同。
-- **《大奥》历史背景**：发言者3介绍该剧三部，前两部对应中国晚明到清初时段；发言者2补充第三部在明治维新之前，是有跨越性的历史剧。
-- **吸引点：严谨精神**：发言者2表示被吸引的是剧中严谨精神，称回头看《三国演义》会看到群众演员笑，但日本剧看不到笑；发言者3称每个人都特别有专业精神，第一集片头将军出场时所有人呈45度鞠躬，场面华丽，一看就不一样。
-- **大奥释义与规矩**：发言者3解释大奥即后宫，日语「奥」指屋子最里处，如「堂奥」「深奥」；发言者2补充另一意思是「一般人不准进去」；发言者3称大奥规矩非常严谨，包括后宫不许进人。
-- **幕府与天皇关系**：发言者2称天皇一直是摆设，实际权力在幕府将军手中，德川家康开创德川幕府后权力集于一人；举例天皇想办活动没钱找将军要，将军不给，活动没办成，天皇为抗议退位。
-- **日本极端精神**：发言者2认为日本文化从头到尾没变，是一种「极端精神」，所有事情要做到尽头；发言者3称这是每个人发自内心的，与中国人不同。
-- **战后经济强国**：发言者3称日本1945年战后用30年成为世界第二经济强国（绝对量，非人均量），是必然而非偶然，源于全民族极端精神，且是强国中唯一没有资源的国家。
-- **中日文化对比**：发言者2称中国文化精神是中庸，不是对也不是错，是「最适合的路」；日本精神恰相反，坚持一个原则，如「鞠一刀」；举例炮手开炮时忘记所有事情只记得把炮开出去，即达最高境界。
-- **忠诚文化体现**：发言者3称日本是忠诚文化的典型国度，靠具体事例而非说教体现；举例《大奥》中阿福25岁进大奥当奶妈，65岁去世，40年完全出于公心，不出于私心，所有人都认为她是楷模。
-- **终身雇佣制**：发言者2称西方经济学家不理解日本终身雇佣制——缺乏竞争应导致效率低下，但日本终身雇佣下员工积极性仍高，是经济学上的奇迹；发言者3补充日本跳槽率最低，每次跳槽都是社会资源浪费。
-- **豆腐厂事例**：发言者3讲述参观日本最底层豆腐厂经历：豆腐规定当天做当天卖，夜里11:45所有人坐好不动看表，12点整一起开始工作，到四点多干完上市，期间无人闲聊。
-- **岛国生存观**：发言者2认为日本是岛国，没有资源、常火山地震，「跑都没地方跑」，人对世界有极强求生欲望或悲观感，必须融入团体按固定规则行事才能生存。
-- **投机取巧无生存环境**：发言者3称日本投机取巧的人没有生存环境，社会文化鄙视使其难以生存；举例日本做绳子做到全日本第一的人，几年内不赚钱铺市场，之后再各加2%赚取利润。
-- **死亡态度分歧**：发言者2认为日本人有「寻死的潜在欲望」，看樱花只看落的那天，对死亡不惧怕甚至有点向往，二战日军暴行是藐视生命的行为；发言者3不同意，认为日本民族不是藐视生命而是重视死亡，经济危机时很多身家万贯的人剖腹自杀。
-## 明朝历史与《明朝那些事》
-- **《明朝那些事》热销**：发言者3称该书发行量排行第一，各报文学类都是第一；发言者1评价「写得好」「写得放松」，发言者3称过去写书的人都「拘着」，对广大读者来说大概是怎么回事就行了。
-- **为何写明史**：发言者2称明史资料最多，历史研究有两个难点：先秦春秋没史料，史记就那么一两篇「都是编的」；明清史料堆得比山还高但同一事件可能有7种不同说法，如黑泽明电影《罗生门》一样。
-- **明朝历史跌宕起伏**：发言者3称明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变、夺门之变，皇上被瓦剌军抓了又扶弟弟上位，「完全构成一个现代版的电视剧」。
-- **推崇朱元璋**：发言者2称推崇朱元璋因他太不容易，从乞丐到推翻元朝当上皇帝，定下明朝规章制度基本无大改动；发言者3称历史上最底层的人坐到最上面「独此一份」，刘邦好歹是村长或乡长。
-- **英雄史观**：发言者3认为人的因素最大，「改变时势一定是出现一个人」；发言者2称朱元璋天分相当高，如《亮剑》中李云龙没上过军事院校但会打仗，是战场上积累经验的天赋。
-- **朱元璋起义的偶然性**：发言者1提到朱元璋好友汤和让他参加起义军，他在庙里犹豫怕被杀头，后因送信被人听到告发，没办法只能去起义；发言者2强调历史最重要的是「一定要弄明白它是发生过的」，旁观者觉得好玩，但当年那是造反，是要掉脑袋的风险。
-- **历史经验教训**：发言者2称「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因为历史事件发生时有背景，你不比前人聪明甚至可能比前人笨，那种情况出现时你也得那么办；史书记载是「照片」，而古人的生活是「录像」，不知道前因后果就不能套用经验。
-- **明末市民生活**：发言者2称明末很多真相被掩盖，市民生活特别轻松舒服，想去哪去哪，江浙一带兴起工商业，给人当雇工活得很滋润，《三言二拍》这类娱乐产品出现说明有养活自己的资本；李自成起义是因陕西一带发生大规模灾荒。
-- **明末艺术与生活**：发言者3称明末工艺变得非常精细，日本派大量工匠来中国交流；文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水，八大山人（朱耷）明末画的都是「翻白眼」，因对社会愤愤不平。
-- **明朝灭亡的蹊跷**：发言者2称1644年李自成军打到京城无人抵抗，有史料记载当时北京闹瘟疫，叫「疙瘩瘟」，即天花；他曾与老师王佩奇交流，认为明朝亡得真蹊跷，「什么坏事儿衰事儿赶上了」。
-- **王朝三百年大限**：发言者3称中国历史王朝约300年是大限，逼近300年就完了；严格讲跨过300年的只有宋朝（南北宋接上，319年），汉朝中间隔断14年不能比，唐朝、明朝、清朝都没跨过；发言者2称一公司成立200多年「够本了」，明朝是几千万人的大摊子。
-## 明朝皇帝趣事与审美
-- **明武宗正德被阻出行**：发言者2称正德皇帝要去江南，大臣全跪金水桥前抗议不让去，皇帝气坏了到锦衣卫打死了十几人，还是不让去；后来打服一批人去了扬州，要东西政府说没有，皇帝不生气说那就回去，还让人把酒席折合成银两带回去。
-- **正德皇帝有城府**：发言者2称正德从江南回来没进京城，在通州先停半天或一天，先派人打探京城里有没有人想搞埋伏搞圈套，说明此人「绝不是史料上所写的那么蠢」。
-- **正德被写坏的原因**：发言者2称正德皇帝被写坏，因接班的嘉靖不是他亲生儿子而是堂兄弟，明武宗实录是嘉靖指派杨廷和等人编的，有偏颇；嘉靖上台后搞大礼仪事件，为给自己父亲争名分折腾了很多人。
-- **豹房实为动物园**：发言者2称豹房不是荒淫场所，真有动物园养了豹子，女人在后宫和豹房「放哪都是一样的」；发言者3称正德是明朝最荒淫的皇帝，但没留种，没有生育能力，对宫廷外女人有兴趣，宫廷内女人禁忌太多。
-- **天启帝爱当木匠**：发言者3称天启帝干完活差大臣去卖，回来还打听卖得怎么样，卖得很好「成就感特大」；发言者3认为这从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然，「所有的偶然中一定有个必然的因素」。
-- **明朝与清朝审美差异**：发言者3称宋明是典型汉人政权、文人政权，审美判断不是表象的；满族是异族，对美的判断是表象的；晚清到民国初年收藏中，外在直观美的东西不值钱，一定是素雅的才值钱。
-- **史官冒死求名**：发言者1提到明朝有些史官把冒死进谏当时尚，「我就是要跟皇帝说点难听的，让你砍我的头，这样我青史留名」；发言者3称这就是文化的力量，超出我们想象。
+## 日本历史剧《大奥》与文化差异
+- **《大奥》概况**：发言者3认为它是大长今以后最有影响的外国剧，发言者2赞同并称其严谨。该剧三部曲，前两部对应中国晚明到清初，后一部在明治维新之前。
+- **大奥释义**：发言者3解释大奥即普通话的后宫，奥指很深的地方、屋子最里处，如「深入堂奥」「道理深奥」；发言者2补充另一意思是「一般人不准进去」。
+- **幕府与天皇关系**：发言者2指出日本天皇一直是摆设，实际权力在幕府将军手中；德川家康开创德川幕府后权力集于一人。天皇曾想办活动因没钱找将军要，将军不给，活动没办成，天皇为此退位抗议。
+- **日本极端精神**：发言者2认为日本文化从头到尾没变，是一种「极端精神」，所有事情要做到尽头；发言者3称这是每个人发自内心的，与中国不同。
+- **战后经济崛起**：发言者3称日本1945年战后用30年成为世界第二经济强国，以绝对量而非人均量计，是强国中唯一没有资源的国家。
+- **终身雇佣制**：发言者2称日本跳槽率最低，终身雇佣制按经济学原理缺乏竞争、应导致效率低下，但日本员工积极性仍高，是西方经济学家不能理解的奇迹。
+- **豆腐厂见闻**：发言者3讲述参观日本最底层豆腐厂，规定当天做当天卖，夜里11:45所有人坐好看表，12点整同时起立开工，到四点多干完上市，无人闲聊。
+- **岛国生存观**：发言者2认为日本是岛国、没有资源、常火山地震，人跑都没地方跑，有极强求生欲望，对世界悲观，必须融入团体按固定规则做事才能生存。
+- **忠诚文化实例**：发言者3举日本做绳子做到全日本第一的人为例，几年内批发送货一分钱不赚，铺平市场后向两边各要2%利润，靠4%赚大钱。
+- **投机者无生存环境**：发言者3称日本投机取巧的人没有生存环境，社会文化鄙视非常难过；发言者1问是否有人坐收渔利时，发言者3答「日本很难」。
+- **死亡观分歧**：发言者2认为日本人藐视生命，二战日军在华暴行即此表现；发言者3不同意，认为日本民族不是藐视生命而是重视死亡，经济危机时身家万贯者剖腹自杀。
+- **文化差异对比**：发言者2称中国文化精神是中庸，不是对错黑白之间而是一条最适合的路；日本精神恰相反，坚持一个原则，如炮手忘记一切只记得开炮即达最高境界。
+- **忠诚文化具体体现**：发言者3称《大奥》第1集阿福25岁进大奥当奶妈、65岁去世，40年完全出于公心不夹杂私利，所有人最终认为她是楷模。
+## 明朝历史与《明朝那些事儿》
+- **明史研究难点**：发言者2称明史资料最多，但一个事件可能有7个不同说法，如同黑泽明电影《罗生门》——一件事5个人看各个不同；先秦则因没史料，如孙武事迹在《史记》只有一两篇，都是编的。
+- **明朝历史跌宕起伏**：发言者3称明朝260多年过程本身跌宕起伏，几次要死没死，如土木堡之变、夺门之变，皇上被瓦剌军抓了又扶弟弟，构成现代版电视剧情节。
+- **推崇朱元璋**：发言者2称朱元璋从乞丐到最后推翻元朝当皇帝，独此一份，刘邦好歹是村长或乡长；明朝规章制度基本由他定下，没有太大改动，是了不起的人才。
+- **英雄史观**：发言者3认为人的因素最大，改变时势一定出现一个人；发言者1称这是英雄史观，有常人不及的地方。
+- **朱元璋起义的逼上梁山**：发言者1提到朱元璋好友汤和让他参加起义军，他在庙里犹豫怕被杀头，后因送信被告发没办法才去；发言者2强调历史最重要的是弄明白这事是真的，当年造反是要掉脑袋的风险事。
+- **明末市民生活**：发言者2称明末很多真相被掩盖，市民生活特别轻松舒服，想去哪去哪，皇册都不用了；江浙一带兴起工商业，给人当雇工活得很滋润，三言二拍这类娱乐产品出现说明有养活自己的资本。
+- **明末艺术繁荣**：发言者3称明末工艺彻底改观、非常精细，日本派大量工匠来交流学习；文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水，到八大山人明末时画的都是翻白眼。
+- **明朝灭亡与瘟疫**：发言者2称1644年李自成军打到京城无人抵抗，因史料记载北京闹瘟疫叫疙瘩瘟（即天花）；他曾与老师王佩奇交流，说明朝亡得蹊跷，什么坏事衰事都赶上了。
+- **王朝300年大限**：发言者3称中国历史王朝300年是大限，逼近300年自己就完了；严格讲跨过300年的只有宋朝（南北宋接上，319年），汉朝中间隔断14年不能比，唐朝明朝清朝都没跨过。
+- **历史教训论断**：发言者2称「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因为历史事件发生时有背景，你不比前人聪明，甚至可能比前人笨，当时那种情况出现你也得那么办。
+- **史书是照片不是录像**：发言者2称史书记载下来的是照片，古人的生活是录像，你不知道那一幕之前和之后是什么，所以不能简单套用经验，套用一定要倒霉。
+- **明代皇帝趣事**：发言者2称明武宗正德要去江南，大臣全跪金水桥前抗议，他气坏到锦衣卫打死了十几个还是不让去；到扬州要东西政府说没有，他让人准备酒席又折合成银两带回去。
+- **正德皇帝被写坏**：发言者2认为正德皇帝绝不是史料写的那么蠢，从江南回来在通州先停半天派人打探京城有无埋伏，很有城府；因明武宗实录是嘉靖指派杨廷和等人编的，嘉靖不是正德亲生而是堂兄弟，为给自己父亲争名分搞大礼仪事件，编修有偏颇。
+- **天启皇帝当木匠**：发言者3称天启皇帝干完活差大臣去卖，回来还打听卖得怎么样，成就感特大；这从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然。
+- **明朝审美与满族对比**：发言者3称宋明是典型汉人文人政权，审美判断不是表象的；满族是异族，对美的判断都是表象的。今天外在美直观能看到的都卖得贵，但晚清到民国初年收藏中这种东西不值钱，一定是素雅的。
+- **史官冒死求名**：发言者1提到明朝有些史官把冒死进谏当时尚，跟皇帝说难听话让砍头以青史留名；发言者3称这就是文化的力量，超出我们想象。
 # 关键引语与金句
 &gt; “慢慢来才是最快的方法。”
-- 背景：发言者2在讨论日本文化中人人按角色做事、不夹杂小聪明时，引用他人之语说明按部就班反而最有效率。
+- 背景：发言者2在讨论日本文化中人人按角色做事、不夹杂个人小聪明时，引述他人观点说明效率与合力的来源。
 &gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
-- 背景：发言者2回应明朝兴亡经验教训能否借鉴时，总结历史经验难以直接套用。
-&gt; “历史它那个事儿发生的时候是有背景的……你甚至可能比前人笨，就是当那种情况出现的时候，你也得那么办。”
-- 背景：发言者2解释为何不能从历史中简单吸取教训，强调后人并不比前人聪明，处境相同也只能同样行事。
-&gt; “史书上记载下来是什么。照片……古人的生活都是录像……在史书上下来的只是一个照片，咔嚓。但你不知道为那一幕之前跟之后是什么。”
-- 背景：发言者2说明历史记载的局限，人们只看到定格瞬间而不知前因后果，因此容易误解历史。
-&gt; “日本的文化跟中国的文化存在一个极大的不同……中国的文化精神是什么？是中庸……但是日本的精神就恰相反，他坚持一个原则。”
-- 背景：发言者2对比中日文化差异，以中庸与坚持原则概括两国精神之别。
-&gt; “所有人按照自己的角色去做自己的事情，最节省成本了……大家都会有一个共同的目标往前走。”
-- 背景：发言者2解释日本社会各司其职形成合力的效率，回应为何日本终身雇佣制下仍保持高积极性。
-&gt; “日本民族的这种极端精神，使一个国家在战后这样一个不利的局面下，只需要30年的时间它进入世界第二经济强国。”
-- 背景：发言者3谈日本战后经济崛起，认为全民族的极端精神使其以绝对量成为世界第二经济强国，且是强国中唯一没有资源的国家。
-&gt; “我们强调一个忠诚可能未必获得一个好处，他强调忠诚最终一定要落到一个好处，所以这个民族才团结。”
-- 背景：发言者3回应日本忠诚文化的讨论，指出日本忠诚最终落实到实际利益，故能凝聚民族。</t>
+- 背景：发言者2回应明朝兴亡经验教训能否被总结运用时，指出历史事件有背景、不能简单套用。
+&gt; “历史它那个事儿发生的时候是有背景的……当那种情况出现的时候，你也得那么办。”
+- 背景：发言者2解释为何不能从历史中直接吸取教训，强调后人并不比前人聪明。
+&gt; “史书上记载下来是什么。照片……古人的生活都是录像。”
+- 背景：发言者2以照片与录像作比，说明史书记录只是瞬间定格，后人看不到事件的前因后果。
+&gt; “日本的文化跟中国的文化存在一个极大的不同……中国的文化精神是什么？是中庸。”
+- 背景：发言者2对比中日文化差异时，以马先生家具店中硬木刻云彩为例，阐释中国的中庸融合之道。
+&gt; “日本人的跳槽率是最低的……每一次跳槽都是社会资源的浪费。”
+- 背景：发言者3在讨论日本忠诚文化时，以跳槽率低作为日本社会指标之一，说明其文化对商业的影响。
+&gt; “日本民族它不是藐视生命，它是重视死亡，它是翻着的。”
+- 背景：发言者3回应发言者2关于日军暴行源于藐视生命的说法，提出日本民族是重视死亡而非藐视生命。
+&gt; “一个乞丐……有这种最底层的人坐到最上面独此一份。”
+- 背景：发言者3在讨论朱元璋时，强调从乞丐到皇帝在历史上独一无二，回应发言者1对朱元璋的推崇。</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>71.3</v>
+        <v>57.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14719/4308</t>
+          <t>14719/3608</t>
         </is>
       </c>
     </row>
@@ -5843,46 +5785,43 @@
       <c r="C17" t="inlineStr">
         <is>
           <t># 就诊概况
-48岁男性患者张学恒，在成都轻工研究所从事科研工作，因上腹反复疼痛4年、近3个月加重，于消化专科初诊。患者主诉心窝部烧灼样疼痛，进食冷硬食物或工作紧张时诱发，近一年内两次出现黑便（分别于一年前和三个月前，每次持续约一个月，每日最多两次，均住院治疗后大便转黄），近两个月呕吐数次，呕吐物为酸味黄水样物，含未消化食物，夜间腹胀时呕吐。近期自行服用奥美拉唑、阿莫西林及医务室胃炎合剂，效果不佳。医生初步考虑上消化道疾病可能，需进一步检查明确诊断，已安排留大便检查及胃镜检查。
+本次门诊由消化专科严医生接诊48岁男性患者张学恒，患者为成都轻工研究所科研人员。就诊形式为初诊，患者因上腹心窝部反复烧灼样疼痛4年、每年春季多发、近3个月持续而来，疼痛进食冷硬或刺激性食物、工作紧张劳累时诱发，可忍受，无夜间痛醒，暖和轻松时无痛；一年前及三个月前各出现一次黑便，每次持续约一个月，每日最多两次，两次均住院检查诊断为大便出血，住院两三天后大便转黄；近两个月呕吐数次，吐出酸味黄水样物，含当日食物，夜间腹胀时呕吐后缓解。患者近期服用国产奥美拉唑（武汉药厂）和阿莫西林，自述增加剂量至每日四五次仍效果不佳。初步考虑上消化道疾病可能，需进一步检查明确，已安排留取大便标本及后天胃镜检查。
 # 病史与背景
-- **现病史**：上腹疼痛4年，每年春季多发，近3个月反复发作；疼痛位于心窝部，呈烧灼感，进食冷硬食物或工作紧张时诱发，可忍受，无夜间痛醒；近三个月大便为黄色，小便正常。
-- **黑便史**：一年前和三个月前各出现一次黑便，每次持续约一个月，每日最多两次，大便呈黑色、像马路上的柏油，形状基本正常；两次均住院治疗，住院后大便转黄，住院时间分别为10天和两三天。
-- **呕吐史**：近两个月呕吐数次，呕吐物为酸味黄水样物，含早晨和中午吃的食物，晚上感觉腹胀时呕吐，吐后舒服，无隔夜食物吐出，呕吐物无红色或黑色。
-- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，之后体检肝功均正常；小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手出现红疹，持续半个月，确诊磺胺药过敏。
-- **预防接种**：按计划进行，近两年所里统一接种乙肝疫苗，上海产，共三针，无不良反应。
-- **系统回顾**：偶有头痛头昏，与休息有关，未就医；双眼近视400度，平时不戴眼镜；偶有口腔溃疡，用贴片治疗；无咳嗽咳痰、无心慌心累；偶有腹泻，与进食不洁食物有关，急性自愈；无关节肌肉疼痛。
-- **个人史**：出生并长期生活在成都，在成都轻工研究所从事科研工作，工作紧张，经常加班熬夜；吸烟史，以前每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝；每天泡茶两次；26岁结婚，爱人及孩子身体健康。
-- **家族史**：父亲76岁，有低血压（90/60mmHg）；母亲75岁，有冠心病，药物控制良好；有一个弟弟，身体健康；婶婶（叔叔的爱人）患胃癌，患者担心自己患病。
+- **现病史**：上腹心窝部烧灼样疼痛反复发作4年，每年春季多发，近3个月持续；进食冷硬、辛辣等刺激性食物或工作紧张劳累时诱发，暖和、轻松时无痛，疼痛可忍受，无夜间痛醒。
+- **黑便史**：一年前及三个月前各出现一次黑便，每次持续约一个月，每日最多两次，大便颜色改变但形状基本正常；两次均住院检查诊断为大便出血，住院两三天后大便转黄。
+- **呕吐**：近两个月呕吐数次，吐出酸味黄水样物，含当日早、中餐食物，夜间腹胀时呕吐后缓解，无隔夜食物及红色、黑色呕吐物。
+- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手出现红疹，持续半个月，确诊磺胺过敏。
+- **个人史**：吸烟史，既往每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝；每天泡茶两次；双眼近视400度，偶有口腔溃疡。
+- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；婶婶（叔叔的爱人）患胃癌，患者担心与此相关，严医生解释无血缘关系，不必过度担心。
 # 诊断与检查结果
-医生初步考虑患者为上消化道疾病，需进一步检查明确诊断，未确诊。患者有两次黑便史，可能存在消化道出血，需留大便检查明确有无出血。患者有婶婶胃癌家族史，虽无血缘关系，但患者有胃癌担忧，医生解释婶婶与患者无血缘关系，无需过度担心。患者担心是否需要手术，医生表示待检查资料全面后再判断，若药物能控制病情则无需手术。
+本次就诊尚未确诊，初步考虑上消化道疾病可能，需进一步检查明确。患者一年前及三个月前两次黑便均经大便检查诊断为大便出血，住院两三天后大便转黄；近三个月无黑便，大便黄色正常，小便正常，体重无明显下降。医生对家族史中婶婶患胃癌的情况进行解释，指出婶婶为叔叔的爱人，与患者无血缘关系，不必过度担心。患者担心是否需手术及出国进修安排，严医生表示待检查资料全面后再判断，若能药物控制则无需手术。
 # 治疗方案与医嘱
-- **检查安排**：留大便检查，以明确有无出血；胃镜预约在后天进行，患者爱人可陪同，胃镜活检后由张大夫查房时讨论结果。
-- **用药**：患者近期自行服用奥美拉唑、阿莫西林及医务室胃炎合剂，效果不佳，医生未开具新药，待检查结果明确后决定治疗方案。
-- **生活方式与饮食**：医生建议患者尽量少抽烟或不抽烟，少喝酒，因吸烟饮酒可能加重胃部疾病；注意休息，避免熬夜。
+- **检查安排**：患者需留取大便标本进行出血相关检查；胃镜预约在后天进行，因患者爱人可请假陪同，胃镜活检后恰逢张大夫查房，便于进一步诊疗。
+- **生活方式与饮食**：建议戒烟限酒，因吸烟饮酒可能加重胃部疾病；注意避免进食冷、硬、辛辣等刺激性食物。
+- **复诊安排**：严医生将总结病情后向上一级张医生（指导教授）汇报，再与患者讨论下一步治疗方案。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 奥美拉唑 | — | — | 口服 | 国产，武汉药厂生产；患者自行服用，效果不佳 |
-| 阿莫西林 | — | — | 口服 | 患者自行服用，效果不佳 |
-| 胃炎合剂 | — | — | 口服 | 医务室配制；患者自行服用，效果不佳 |
+| 奥美拉唑 | — | 每日四五次（自述加量后） | 口服 | 国产，武汉药厂；自述加量后效果仍不佳 |
+| 阿莫西林 | — | — | 口服 | — |
 # 复诊与预警信号
 ## 复诊与随访安排
-- **胃镜检查**：预约在后天进行，患者爱人可陪同，胃镜活检后由张大夫查房时讨论结果。
-- **大便检查**：留大便检查，以明确有无出血。
-- **病情汇报**：医生将总结病情向张医生汇报，待汇报后再与患者商量下一步处理意见。
+- **胃镜检查**：预约在后天进行，因患者爱人可请假陪同；胃镜活检后恰逢张大夫查房，便于进一步诊疗。
+- **大便检查**：患者需留取大便标本进行出血相关检查。
+- **病情汇报**：严医生将总结病情后向张医生（指导教授）汇报，再讨论治疗方案。
 ## 预警信号
-- ⚠️ 黑便：患者曾两次出现黑便，若再次出现需及时就医。
-- ⚠️ 呕吐物带血：若呕吐物出现红色或黑色，需立即就医。
+- ⚠️ 再次出现黑便或大便带血。
+- ⚠️ 呕吐物带红色或黑色。
 ## 需要观察的变化
-- 观察大便颜色，若出现黑便或便血需提前联系。
-- 观察腹痛变化，若疼痛加重或出现新症状需及时就医。</t>
+- 观察大便颜色变化，若出现黑便需及时就医。
+- 观察腹痛发作频率与程度变化。</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>51.9</v>
+        <v>49.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8519/1754</t>
+          <t>8519/1565</t>
         </is>
       </c>
     </row>
@@ -6837,63 +6776,62 @@
       <c r="C18" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审，由最高人民法院依法组成合议庭公开开庭审理。庭审围绕三个争议焦点展开法庭调查与辩论：国开行抵押权是否善意取得及融资租赁登记性质、罚息与复利计算、东源煤电是否应连带给付违约金。各方充分发表意见后，合议庭休庭评议并提出调解方案，各方均无异议并签字确认，法院当庭确认调解协议并出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审案，由最高人民法院组成合议庭公开开庭审理。庭审围绕动产抵押权与融资租赁所有权冲突、罚息复利计算、违约金连带责任三个争议焦点展开调查与辩论，各方充分发表意见后，合议庭在查明事实、分清是非的基础上提出调解方案，各方无异议并签署调解协议，法院出具调解书。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国家开发银行） | 请求撤销一审判决，改判支持其利息、罚息、复利计算主张及违约金请求 | 主张其审查义务仅限于抵押人曲靖电力公司，已尽合理审慎义务，构成善意取得；罚息、复利计算有合同依据；东源煤电未配合办理账户管理及柜台签约手续，构成违约，应支付千分之一违约金 |
-| 被上诉人（云南东源电力股份有限公司、云南东源曲靖电力有限公司） | 请求驳回上诉，维持一审判决 | 主张国开行宣布贷款提前到期未给合理期限，不符合合同约定；罚息不应作为复利计算基数；国开行未举证东源煤电违约行为，且未按合同约定发出限期纠正通知 |
-| 被上诉人（招银金融租赁有限公司） | 请求驳回上诉，维持一审判决 | 主张国开行未在抵押时查询融资租赁登记，不构成善意；东源煤电出资行为系无权处分，因招银租赁2012年已取得设备所有权；国开行2015年抵押登记在后 |
+| 上诉人（国家开发银行） | 请求撤销一审判决相关部分，改判支持其罚息、复利、违约金主张；确认其对案涉设备享有抵押权。 | 主张其抵押登记针对曲靖电力公司设备，与招银租赁设备不同；已尽审慎审查义务，构成善意取得；利息计算至2017年12月20日，罚息自2018年6月13日起算，复利按合同第六条第四款约定计算；东源煤电违约应支付千分之一违约金。 |
+| 被上诉人（云南东源电力股份有限公司、云南东源曲靖电力有限公司） | 请求驳回上诉，维持一审判决；认为罚息不应作为复利计算基数，提前到期通知未给合理期限，违约金主张无事实依据。 | 主张2015年12月2日邮件已告知设备抵押情况，国开行应尽注意义务；依据人民币利率管理规定第21条及最高法判例，罚息不能作为复利计算基数；国开行未举证违约事实，且未发出限期纠正通知。 |
+| 被上诉人（招银金融租赁有限公司） | 请求驳回上诉，维持一审判决；主张其对案涉6项设备享有所有权，国开行不构成善意取得。 | 主张国开行未在抵押时查询融资租赁登记，不构成善意；东源煤电出资行为系无权处分；招银租赁2012年即取得设备所有权；融资租赁登记非强制且不产生物权效力。 |
 # 举证与法庭调查
 ## 举证与质证
-- **国开行提交**：2018年9月对曲靖电力公司的租赁查询证书，证明其已尽查询义务；招银租赁质证认为该查询证书不符合要求，依据2014年93号中国人民银行关于融资租赁登记系统规定，国开行在抵押时点未进行相应查询。
-- **国开行提交**：工商部门出资证明及四冶合成58亿材料，证明已对设备所有权尽审慎审查义务；招银租赁认为工商登记公示的是出资行为而非动产公示，东源煤电出资行为系无权处分。
-- **国开行提交**：2018年再次核查曲靖电力公司名下融资租赁情况的核查表（见证据108页），显示仍无融资租赁登记；招银租赁认为该核查表不符合要求。
-- **招银租赁提交**：回租设备清单（一审证据7页），仅载明设备名称和生产厂家，未提及型号；国开行质证认为无法据此识别设备唯一性，且清单提示2012年3月1日，而抵押设备铭牌生产日期均在2013年以后，看不出是同一设备。
-- **招银租赁提交**：2013年和2015年审计报告（见证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行认为该报告已载明设备出资事项，招银租赁知道或应当知道设备出资情况。
-- **东源公司提交**：2015年12月2日邮件及融资情况统计表，证明已告知国开行设备存在融资租赁；国开行质证认为该邮件系常规贷后审查，正文及附表均无融资租赁情形记载，统计表中招银租赁一栏记载的抵押类型为不动产抵押，与融资租赁概念不同，不能得出已告知的结论。
+- **国开行提交证据**：2018年6月13日向东源煤电、东源煤业发送的偿还贷款本金函件，证明其已宣布贷款提前到期，罚息应自2018年6月13日起算。东源公司质证认为，该函件未给合理期限，不符合合同约定。
+- **国开行提交证据**：2018年9月融资租赁查询证书（第五组证据第一项），证明其已尽查询义务。招银租赁质证认为，该查询证书不符合2014年93号文规定，国开行在抵押时点未进行相应查询。
+- **国开行提交证据**：工商部门出资证明、四冶合成58亿材料、人民银行出具的相关情况，证明其对设备所有权已尽审慎审查义务。招银租赁质证认为，工商登记公示的是出资行为而非动产所有权，东源煤电出资行为系无权处分。
+- **国开行提交证据**：2018年对曲靖电力公司名下融资租赁情况的核查表（证据108页），证明核查时无融资租赁登记。招银租赁质证认为，该核查表不符合要求。
+- **招银租赁提交证据**：回租设备清单（一审证据7页），载明设备名称、生产厂家，但未载明型号。国开行质证认为，该清单无法证明设备唯一性，且铭牌生产日期均在2013年以后，与清单提示的2012年3月1日不符。
+- **招银租赁提交证据**：2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴。国开行质证认为，该报告已载明设备出资事项，招银租赁应当知道设备出资情况。
+- **东源公司提交证据**：2015年12月2日邮件及融资情况统计表，证明其已告知国开行设备抵押情况。国开行质证认为，邮件正文及附表均未提及融资租赁情形，统计表中招银租赁一栏记载的抵押类型为不动产抵押，与融资租赁概念不同，无法得出已告知的结论。
 ## 证人、鉴定与其他来源陈述
-- **评估报告**：明确曲靖电力公司拥有的在建工程价值5.7亿元，机械设备价值5.1亿元；国开行主张该报告已确认资产存在，且企业未纳入资产负债表不等于不拥有资产。
-- **上海中院一审判决**：仅限东源煤电对相应设备的返还义务，未明确确认设备所有权归招银租赁所有；国开行主张该判决与本案抵押权审理不冲突。
+- **评估报告**：评估报告明确曲靖电力公司拥有的在建工程价值5.7亿元，机械设备价值5.1亿元。国开行代理人引用该报告主张设备资产存在。
+- **审计报告**：招银租赁一审提交的2013年、2015年审计报告（证据82页、95页）载明曲靖电力公司注册资本4亿元且已实缴。
 ## 法官询问
-- **审判员询问国开行**：贷款前审查风险控制所需资料中，内部是否有规定必须查询融资租赁登记，未查到是否需将未查到单子作为风控材料；国开行代理人回答：按央行规定需查询该系统，但当时未保留筛查记录，因未查到结果故无必要保留。
-- **审判员询问国开行**：认为查询了电力公司登记信息、未查到设备融资租赁登记结果，以此免责的逻辑；国开行代理人回答：作为金融机构按央行规定查询融资租赁系统，因设备系通用设备无法逐一查询，且抵押人系曲靖电力公司，查询后系统无任何融资租赁记载，至今亦无，故无过失。
-- **审判员询问招银租赁**：融资租赁登记系统中设备唯一标识码是否必填项；招银租赁代理人回答：唯一标识码非必填项，因设备不像汽车有发动机号，无法唯一标识。
-- **审判员询问国开行和招银租赁**：央行融资租赁登记查询方式能否保证查询到登记结果；国开行代理人回答：目前只能通过查询单位名称方式查询；招银租赁代理人回答：可通过公司名称或设备情况两种方式查询，但设备查询涉及种类物区分问题，需登记因素明确唯一性。
-- **审判员询问国开行和招银租赁**：查询通知规定银行业办理抵押前需查询，违反规范会导致何种后果；国开行代理人回答：这是基本查询义务，依据最高人民法院融资租赁司法解释第九条第三款，金融机构取得善意权利应查询融资租赁情况；招银租赁代理人回答：这是对银行业的严格要求，未查询即违反行业规范，但处罚程度因案而异。
-- **审判员询问**：动产融资租赁因属性问题产生所有权与占有分离，融资租赁司法解释第九条第一款规定善意取得情形，第二款列举排除善意取得情形，包括查询问题；各方就查询义务范围、举证责任分配发表意见。
-- **审判员询问**：案涉动产设备在国家无统一登记制度情况下，如何看待不同登记机构产生登记瑕疵；国开行代理人回答：涉及人民银行融资租赁登记系统与动产抵押登记冲突，系统信息不完整是整体问题，可能导致多重动产抵押风险；东源公司代理人表示非专业机构，无法提供建议；招银租赁代理人建议从立法层面统一金融主体要求，发挥行业协会作用，并指出登记平台不统一、主管机构不一致等问题。
+- **审判员询问**：央行融资租赁登记查询方式能否保证查询到登记结果？国开行代理人答：目前只能通过查询单位名称方式查询；招银租赁代理人答：可通过公司名称或设备情况两种方式查询，但设备查询涉及种类物区分问题。
+- **审判员询问**：国开行贷款前审查中，内部是否有规定必须查询融资租赁登记，未查到需将未查到单子作为风控材料？国开行代理人答：办理动产抵押时需筛查系统，但因无查询结果，未保留筛查记录。
+- **审判员询问**：国开行认为查询了电力公司登记信息，未查到设备融资租赁登记结果，以此免责的逻辑？国开行代理人答：作为金融机构按央行规定查询融资租赁系统，因设备为通用设备无法逐一查询，且查询曲靖电力公司无融资租赁记录，至今仍无记录，故无过失。
+- **审判员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁代理人答：不是必填项，因设备不像汽车有发动机号，无法唯一标识。
+- **审判员询问**：查询通知规定银行业办理抵押前需查询，违反规范会导致什么后果？国开行代理人答：这是基本查询义务，根据最高法融资租赁司法解释第九条第三款，金融机构取得善意权利应查询融资租赁情况。
+- **审判员询问**：若通过其他渠道知道抵押设备存在租赁，是否仍需查询？招银租赁代理人答：仍需通过央行系统查询，因其他方式无法证明，只有央行系统是确定标准。
+- **审判员询问**：如何看待因不同登记机构产生登记瑕疵？国开行代理人答：人民银行融资租赁登记系统与动产抵押登记系统相互隔离、信息不流畅，导致多重抵押风险；招银租赁代理人答：规范不统一、登记机构不统一导致信息不对称，应从立法层面统一要求。
 ## 争议焦点与辩论
-- **争议焦点一：国开行抵押权是否善意取得及融资租赁登记性质**
-  - **国开行主张**：其审查义务仅限于抵押人曲靖电力公司，已尽合理审慎义务，构成善意取得；融资租赁登记系行业性规范，非法定登记，不产生物权效力。
-  - **招银租赁主张**：国开行未在抵押时查询融资租赁登记，不构成善意；东源煤电出资行为系无权处分，因招银租赁2012年已取得设备所有权，国开行2015年抵押登记在后。
-  - **东源公司主张**：2015年12月2日邮件已告知设备融资租赁情况，国开行作为专业金融机构应尽注意义务。
-  - **国开行反驳**：该邮件系贷后审查材料，未明确告知融资租赁情形；设备系通用设备，无唯一标识，无法逐一查询。
-  - **国开行主张**：利息计算至2018年6月12日合计2179.572708万元，罚息自2018年6月13日至2019年2月19日合计4105.057957万元，复利自2018年3月21日至2019年2月19日合计191.8206万元；罚息复利有合同依据，且一审已支持罚息复利，依不告不理原则应予支持。
-  - **东源公司主张**：国开行宣布贷款提前到期未给合理期限，不符合合同约定；罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条及最高人民法院2015年、2016年判例；复利再计算复利无合同依据。
-- **争议焦点三：东源煤电是否应连带给付违约金**
-  - **国开行主张**：依借款合同第24条第三项，东源煤电应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台签约手续，构成违约。
-  - **东源公司主张**：国开行未举证东源煤电违反柜台协议；未按合同约定发出限期纠正通知，主张违约金不符合合同约定。
+- **争议焦点一：动产抵押权与融资租赁所有权冲突**
+  - **国开行主张**：其抵押登记针对曲靖电力公司设备，与招银租赁设备不同；已尽审慎审查义务，构成善意取得；融资租赁登记属行业强制规范，非法定登记。
+  - **招银租赁主张**：国开行未在抵押时查询融资租赁登记，不构成善意；东源煤电出资行为系无权处分；招银租赁2012年即取得设备所有权。
+  - **东源公司主张**：2015年12月2日邮件已告知设备抵押情况，国开行作为专业金融机构应尽注意义务。
+  - **国开行主张**：利息计算至2017年12月20日，罚息自2018年6月13日起算，复利按合同第六条第四款约定计算。
+  - **东源公司主张**：罚息不应作为复利计算基数，依据人民币利率管理规定第21条及最高法判例；提前到期通知未给合理期限，不符合合同约定。
+  - **国开行主张**：依据合同第24条第三项，东源煤电违约应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台签约手续，构成违约。
+  - **东源公司主张**：国开行未举证东源煤电违反柜台协议；未发出限期纠正通知，不符合合同约定。
 # 庭审结果
-- **争议焦点一**：国开行抵押权是否善意取得及融资租赁登记性质。
-- **争议焦点二**：罚息、复利计算。
-- **争议焦点三**：东源煤电是否应连带给付违约金。
-- **调解结果**：经合议庭主持调解，各方达成调解协议，均无异议并签字确认，法院当庭确认调解协议并出具调解书。
-  - 确定国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元。
-  - 确定招银租赁对涉案六项设备享有所有权，对应债权1377.4137万元。
-  - 确定国开行对93项设备有抵押权，招银租赁对六项设备有所有权。
-  - 招银租赁和国开行对案涉全部发电设备整体盘活处置，变现款各50%，费用各担50%。
-  - 若司法变现不能，双方放弃设备权益，由东源曲靖电力自主生产经营。
-  - 各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认。
+- **争议焦点一**：动产抵押权与融资租赁所有权冲突。国开行主张其抵押登记针对曲靖电力公司设备，与招银租赁设备不同，且已尽审慎义务，构成善意取得；招银租赁认为国开行未在抵押时查询融资租赁登记，不构成善意。
+- **争议焦点二**：罚息、复息计算。国开行主张利息计算至2017年12月20日，罚息自2018年6月13日起算，复利按合同约定计算；东源公司认为罚息不应作为复利计算基数，且提前到期通知未给合理期限。
+- **争议焦点三**：违约金连带责任。国开行主张东源煤电违约应支付千分之一违约金；东源公司认为国开行未举证违约事实，且未发出限期纠正通知。
+- **调解结果**：经本院主持调解，各方当事人自愿达成调解协议，法院予以确认并出具调解书。
+  - 确认国开行对93项设备有抵押权，招银租赁对6项设备有所有权。
+  - 国开行债权扣除破产中已清偿本金后，利息、罚息、复利合计6474.4513万元。
+  - 招银租赁对6项设备享有所有权，对应债权1377.4137万元。
+  - 设备整体盘活处置，变现款双方各50%，费用各担50%。
+  - 若变现不足，招银租赁债权按破产重整计划预留方案实现。
+  - 各方对一审判决第二项、第四项无争议。
   - 一审诉讼费中国开行诉请部分按一审判决执行，招银租赁诉请部分由二审法院按规定确定，二审诉讼费由本院依法确定。</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>73.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30731/3559</t>
+          <t>30731/3458</t>
         </is>
       </c>
     </row>
@@ -7000,50 +6938,48 @@
       <c r="C19" t="inlineStr">
         <is>
           <t># 候选人概况与面试岗位
-考生为一名文科生，未提及学历、专业及工作经历。本次面试为公务员结构化面试，共四道题，时长20分钟，由面试官主持并计时，考生逐题作答。考生作答内容完整，覆盖各题要点：第一题以绳子对骏马、风筝、陀螺的作用为引，阐述对公务员工作的启示；第二题模拟市政府办公室工作人员小王，调研本市AI企业发展状况与服务需求；第三题模拟服务标兵小王，现场答复记者关于排水管道反复堵塞的投诉；第四题从公共服务角度谈道路改造和雨污分流工程引发居民不满的处理思路。面试官在第四题作答中途提示剩余3分钟，考生在时限内完成全部作答，无补充内容。
+考生为文科生，未提及学历、专业与工作经历。本次为公务员结构化面试，时长20分钟，共4道题，由面试官主持、计时员计时，考生逐题作答。考生对四题均完成作答，作答内容完整，面试官未作当场点评，仅在第四题作答期间提示剩余3分钟，并在结束后询问是否有补充，考生回答无补充。
 # 面试问答纪要
 ## 第1题（综合分析能力）
 - 题目：以绳子对骏马、风筝、陀螺的不同作用为引，谈对做好公务员工作的启示。
-- 作答要点：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；公务员需自我反省，引用曾子“吾日三省吾身”；单位应形成紧张、活泼、团结的风气，同事间比能力和效率；治国理政中权利和责任是风筝的“风”和“绳子”，需建立权利清单和责任清单；陀螺的“连轴转”体现公职人员的责任感和成就感。
+- 作答要点：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；引用曾子“吾日三省吾身”强调自我反省；单位应形成紧张、活泼、团结的风气，同事间比能力和效率；治国理政中权利和责任是风筝的“风”和“绳子”，需建立权利清单和责任清单；陀螺的“连轴转”体现公职人员的责任感和成就感。
 ## 第2题（组织协调能力）
-- 题目：作为市政府办公室工作人员小王，调研本市AI企业发展状况和服务需求，为出台扶持政策提供依据。
-- 作答要点：前期准备包括补课学习AI知识、学习兄弟城市经验、查阅国务院和省厅指导意见；调研分三部分：市场状况、服务需求、管理措施；方法包括与企业对接、阅读发展报告、制定调查问卷、召开座谈会；服务需求侧重人才引进、政策倾斜、用地审批、人才培养机制；管理措施需关注AI发展中的问题，如共享充电宝信任危机，需及时纠偏。
-## 第3题（应急处理与沟通能力）
-- 题目：作为服务标兵小王，现场模拟答复记者关于排水管道反复堵塞的投诉。
-- 作答要点：承认工作失职，说明管道为90年代修建、老城区改造难度大，夏天用水高峰问题集中；已联系维修师傅，将问题汇报上级，计划通过城市综合保障工程完善硬件；请求媒体解释政府难处，并给予改进机会。
-## 第4题（公共服务意识）
-- 题目：从公共服务角度谈道路改造和雨污分流工程引发居民不满的社会矛盾处理思路。
-- 作答要点：区分主要矛盾（时间需求）与次要矛盾（噪音、出行、舆论）；措施包括督促施工方加快进度、使用防噪墙和洒水降尘、建议替代路线、交通广播推荐路线、鼓励公交出行、增加公交班次；计划通过网络公告公开透明说明政府举措，获得市民理解。
+- 题目：作为市政府办公室工作人员小王，负责调研本市AI企业发展状况和服务需求，为政府出台扶持政策提供依据。
+- 作答要点：前期准备包括学习兄弟城市调研经验、查阅国务院和省厅关于人工智能的指导意见；调研分三部分：客观市场状况、服务需求、管理措施；方法包括对接企业阅读发展报告、制定调查问卷（请专家修改完善）、召开座谈会；服务需求侧重人才引进、政策倾斜、用地审批、人才培养机制；管理措施关注人工智能发展中的问题（如共享充电宝信任危机）并及时纠偏。
+## 第3题（应急处理能力）
+- 题目：作为市级服务标兵小王，现场模拟答复记者关于地下排水管道疏通后又堵上的投诉。
+- 作答要点：解释管道为90年代修建，老城区改造难度大，夏季用水高峰问题集中；承认工作失职，请求媒体给予改进机会；已联系维修师傅准备维修，并将管道硬件问题汇报上级，计划通过城市综合保障工程完善基础设施。
+## 第4题（公共服务能力）
+- 题目：从公共服务角度谈谈处理道路改造和雨污分流工程引发社会矛盾的思路。
+- 作答要点：指出主要矛盾是时间上的矛盾（过去城市发展滞后、需求跟不上），次要矛盾包括噪音污染、出行问题和舆论问题；措施包括督促施工方加快进度、使用防噪墙和洒水降尘、建议出行便道、交通广播推荐路线、加强宣传引导公交出行并增加公交班次；最后以公告形式在网络发布，公开透明表达政府举措。
 # 能力评估
+本栏明细由下表承载。
 | 评估维度 | 推荐评级 | 评估依据（具体事例） |
 | --- | --- | --- |
-| 综合分析能力 | — | 第一题中从绳子对骏马、风筝、陀螺的不同作用展开联想，引用曾子名言，提出自我反省、单位风气、权责清单等观点，体现对公务员工作的理解。 |
-| 组织协调能力 | — | 第二题中提出调研分前期准备、市场状况、服务需求、管理措施四部分，方法包括补课学习、查阅文件、企业对接、调查问卷、座谈会等，覆盖全面。 |
-| 应急处理能力 | — | 第三题中承认工作失职，说明管道为90年代修建、老城区改造难度大，已联系维修并汇报上级，计划通过城市综合保障工程完善硬件，并请求媒体解释政府难处。 |
-| 公共服务意识 | — | 第四题中区分主要矛盾与次要矛盾，提出督促施工进度、防噪降尘、替代路线、交通广播、增加公交班次、网络公告等措施，体现公共服务导向。 |
+| 综合分析能力 | 良 | 第一题中能由绳子对骏马、风筝、陀螺的不同作用引申出自我鞭策、权责平衡、责任驱动等启示，并引用曾子名言，但部分表述稍显冗长。 |
+| 组织协调能力 | 良 | 第二题中调研步骤清晰，涵盖前期准备、方案制定、实施调研，方法具体（对接企业、问卷、座谈会），但未提及调研时间安排和人员分工。 |
+| 应急处理能力 | 良 | 第三题中能解释管道问题原因、承认失职、说明维修和长远措施，但未提及如何核实记者投诉的具体情况。 |
+| 公共服务意识 | 良 | 第四题中能区分主要矛盾和次要矛盾，提出多项具体措施（防噪墙、洒水降尘、公交引导等），并强调公开透明沟通。 |
 # 综合素质
 ## 突出亮点
-- **自我反思意识**：第一题中引用曾子“吾日三省吾身”，强调公务员应多反省工作中的失误和拖延，体现自我提升意识。
-- **权责平衡观念**：将风筝的“绳子”类比治国理政中的责任，提出建立权利清单和责任清单，体现对权责关系的理解。
-- **调研方法多样**：第二题中提出补课学习、查阅文件、企业对接、调查问卷、座谈会等多种调研方式，覆盖客观与主观两方面。
-- **承认失职并积极补救**：第三题中承认工作失职，说明已联系维修并汇报上级，计划通过城市综合保障工程完善硬件，体现担当。
-- **矛盾分层处理**：第四题区分主要矛盾与次要矛盾，提出针对性措施，体现系统思维。
+- **自我反思意识**：引用曾子“吾日三省吾身”，强调公务员应多反省工作中的失误和拖延。
+- **权责平衡观念**：将权利和责任比作风筝的“风”和“绳子”，提出建立权利清单和责任清单。
+- **调研方法具体**：第二题中提出对接企业阅读发展报告、制定调查问卷、召开座谈会等具体方法，并请专家修改问卷。
+- **应急处理态度**：第三题中承认工作失职，同时说明已联系维修师傅并汇报上级，体现负责态度。
 ## 潜在风险点
-- **知识储备不足**：第二题中自述为文科生，对人工智能存在知识盲区，需利用课余时间补课，可能影响调研深度。
-- **表述口语化**：作答中出现“实事求是地讲”“咱们”等口语化表达，可能影响正式场合的严谨性。
-- **时间管理**：第四题作答中途被提示剩余3分钟，虽完成作答，但时间分配略显紧张。
+- **知识盲区**：考生自述为文科生，对人工智能存在知识盲区，需利用课余时间补课。
+- **时间管理**：第四题作答期间被提示剩余3分钟，可能影响后续作答完整性。
 ## 推进建议
-- **加强专业知识学习**：针对AI等高新技术领域，建议系统学习相关政策和技术知识，提升调研专业性。
-- **规范语言表达**：在正式场合注意用词严谨，减少口语化表达，增强说服力。
-- **优化时间分配**：答题时合理分配每题时间，避免因时间不足影响后续作答质量。</t>
+- **加强专业学习**：针对AI调研任务，建议考生持续补充人工智能领域知识，以提升调研专业性。
+- **优化时间分配**：面试中注意控制每题作答时间，避免因超时影响整体表现。</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>60.4</v>
+        <v>58.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5808/2027</t>
+          <t>5808/1711</t>
         </is>
       </c>
     </row>
@@ -7112,71 +7048,91 @@
       <c r="C20" t="inlineStr">
         <is>
           <t># 参观概况
-本次参观为故宫博物院游览讲解，主讲人于视频中依次介绍午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、御花园等主要景点，涵盖各建筑的历史功能、典故与建筑细节，并穿插明三暗五、文东武西、正大光明牌匾立储等知识。讲解同时总结三条游览路线，分别适合全天、半天与约2小时的行程，并标注故宫内七个免费盖章点及各店印章差异。整体过程以中轴线为主干、东西两路为辅，兼顾历史讲解、文创体验与路线规划，形成一套完整的故宫保姆级游览攻略。
+本次参观为故宫博物院一日深度游览，核心主题是故宫主要景点讲解与游览攻略分享。游览沿中轴线依次经过午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫，再向西至储秀宫、慈宁宫、寿康宫，随后经断虹桥、武英殿、文华殿、箭亭，参观钟表馆与珍宝馆，最后经东筒子夹道、延禧宫、景仁宫抵达御花园，从神武门结束。讲解穿插历史典故与建筑功能，如午门“明三暗五”结构、太和殿典礼功能、乾清宫立储诏书秘密等，并介绍了故宫内七个免费盖章点及三条不同时长的游览路线。
 # 核心看点与讲解
-- **午门**：排队检票处，明朝皇帝在此杖打犯错大臣，清朝皇帝在此举行颁朔之礼。门洞呈明三暗五格局，中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名可出一次，两侧门走皇亲国戚和文武百官。
-- **太和门广场**：眼前有五座金水桥，皇帝走中间，黄金国器走挨着中间两座桥，文武百官走最边上。太和门是明朝皇帝御门听政的上朝之处，门口铜狮子为故宫六对铜狮中最大的一对，脚踩寰宇象征权力。
-- **太和殿**：即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封，文武百官在太和殿广场高呼万岁。百官站位遵循文东武西，西边弘义阁为皇帝银库，东边体仁阁为缎库。
+- **午门**：排队检票处，明朝皇帝在此杖打犯错大臣，清朝皇帝在此颁发次年历书（颁朔之礼）。门洞呈明三暗五结构，中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名可出一次，旁门走皇亲国戚和文武百官。
+- **太和门广场**：眼前有五座金水桥，皇帝走中间，皇亲国戚走挨着中间的两座，文武百官走最边上。
+- **太和门**：明朝皇帝在此御门听政，即上朝的地方。门口铜狮子为故宫六对铜狮中最大的一对，脚踩寰宇象征权力，建议单独拍照，不要站在其底下合影。
+- **太和殿**：即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封。文武百官在太和殿广场向皇帝高呼万岁，站位遵循文东武西——文官站东边，武官站西边。
+- **体仁阁与弘义阁**：东边体仁阁为缎库，西边弘义阁为银库，是皇帝的「内库」（原文如此，主讲人表述为「皇上的内库」）。
 - **中和殿**：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再前往太和殿。
-- **保和殿**：从乾隆五十四年开始作为科举殿试考场。东北角汉字馆有4枚免费印章，可购买《紫禁城100》现场盖章，各店印章不同，购买后不能跨店盖章。
-- **乾清门**：过了此门即后宫生活区域，皇帝在此上早朝。东边九卿直房为大臣等待召见处，西边为军机处。门口狮子耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
-- **乾清宫**：皇帝睡觉之处，据说有27张龙床以防刺客。牌匾「正大光明」后藏立储诏书，皇帝写两份诏书，驾崩后对比验证是否被动过手脚。门口有铜鹤铜龟及紫禁城最小宫殿社稷江山金殿，提醒皇帝把江山社稷放在第一位。
+- **保和殿**：从乾隆五十四年开始作为科举殿试考场。东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》现场盖章，且可邮寄到家或自行带走。
+- **乾清门**：过此门即后宫生活区域。东边九卿直房为等级高的大臣等待召见处，西边为军机处。门口铜狮子耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
+- **乾清宫**：皇帝平时睡觉的地方，据说有27张龙床以防刺客。牌匾「正大光明」后藏立储诏书，皇帝写两份诏书，驾崩后对比验证是否被动过手脚。门口有铜鹤铜龟及社稷江山金殿——紫禁城里最小的宫殿，提醒皇帝把江山社稷放在第一位。
 - **交泰殿**：殿内放有25块传国玉玺。
 - **坤宁宫**：皇后住所，明朝所有皇后都住于此。东北角文创店有5枚免费印章。
-- **储秀宫**：慈禧住了20多年的地方，现为慈禧五十大寿时期原状陈列，慈禧因其子在此出生而偏爱此处。旁边文创店有3枚免费印章。
-- **翊坤宫与永寿宫**：翊坤宫和永寿宫位于储秀宫以南，永寿宫西边为东西六宫中唯一被称为殿的太极殿。
-- **慈宁宫与寿康宫**：慈宁宫为康熙给奶奶孝庄皇太后修建的养老院，旁边寿康宫为甄嬛居住之处。附近冰窖书吧有3枚免费印章，印章造型有批折子之感。
-- **断虹桥**：网红打卡地，桥上有形态各异的石狮子，最有名的为武当狮。往西为武英殿，后改陶瓷馆，目前关闭状态。
-- **文华殿**：位于东边，与西边武英殿对应文东武西。主讲人去时未开放，据说现有一个展览。
-- **箭亭**：清朝皇帝及子孙练习骑马射箭之处，旁边商店可购买文创雪糕。
-- **钟表馆**：展示那个年代的钟表造型，令人开眼界。
-- **珍宝馆**：即宁寿全宫，乾隆给自己修建的养老院，退休后未放权仍照常上朝。皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫。馆内宝贝惊艳但游客众多，尤其凤冠展区拥挤。门口为我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头，据说是当年烧制琉璃损坏后工匠为保命用木头刷白漆以假乱真。
-- **养性殿与乐寿堂**：养性殿后为乐寿堂，是故宫内唯一能进去参观的皇家寝室，有二龙仙楼设计。再往后为珍妃井，现上头为井口石，珍妃并非从那个小眼进去。珍宝馆出口商店有3枚免费印章。
-- **东筒子夹道**：长长的夹道，拍照非常出片，沿路往南拐弯即到延禧宫。
-- **延禧宫与景仁宫**：延禧宫为网红打卡地，旁边景仁宫为甄嬛被封熹妃时所住，珍妃也住过。
-- **御花园**：内有钦安殿供奉真武大帝，紫禁城靠山景山从天上看酷似闭目盘坐人像，有人说造型即真武大帝。
-- **神武门**：故宫北门，游览终点。出门左手边角楼咖啡有2枚免费印章，故宫文创也有2枚免费印章。
+- **储秀宫**：慈禧居住20多年的地方，现为慈禧五十大寿时期原状陈列，慈禧因儿子在此出生而偏爱此处。旁边文创店有3枚免费印章。
+- **翊坤宫与永寿宫**：永寿宫西边为东西六宫中唯一被称为殿的太极殿。
+- **慈宁宫与寿康宫**：慈宁宫为康熙给奶奶孝庄皇太后修建的养老院，寿康宫为甄嬛（原文如此）居住地。
+- **冰窖书吧**：内有3枚免费印章，印章造型有批折子的感觉。
+- **断虹桥**：桥上有形态各异的石狮子，最有名的是「武当狮」（原文如此）。
+- **武英殿**：后改为陶瓷馆，目前关闭状态，只能在门口观看。
+- **文华殿**：与武英殿对应文东武西格局，主讲人去时未开放，据说现有一个展览。
+- **箭亭**：清朝皇帝及子孙练习骑马射箭的地方，旁边商店可购买文创雪糕。
+- **钟表馆**：展示那个年代的钟表造型。
+- **珍宝馆**：即宁寿全宫，是乾隆给自己修建的养老院，乾隆退休后未放权仍照常上朝。皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫。馆内虽称馆但不是单独展厅，院子周围屋子均可参观，游客众多，尤其凤冠展区拥挤。门口为我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据说是当年烧制琉璃时弄坏一块，工匠为保命用木头刷白漆以假乱真。
+- **养性殿与乐寿堂**：养性殿后有乐寿堂，是故宫里唯一能进去参观的皇家寝室，内有二龙仙楼设计。
+- **珍妃井**：当年慈禧把珍妃丢进去的地方，现上头放的为井口石，珍妃并非从那个小眼进去。珍宝馆出口右手边商店有3枚免费印章。
+- **东筒子夹道**：长长的夹道，拍照非常出片。
+- **延禧宫与景仁宫**：延禧宫为网红打卡地，景仁宫为甄嬛被封熹妃时所住，珍妃也住过。
+- **御花园**：内有钦安殿，供奉真武大帝，与北边景山酷似闭目盘坐人像的造型相呼应。
+- **神武门**：故宫北门，出门左手边有两个盖章点——角楼咖啡2枚免费印章、故宫文创2枚免费印章。
 # 互动与体验
-- **盖章体验**：保和殿东北角汉字馆有4枚免费印章，可现场购买《紫禁城100》并由工作人员盖章，据说此处印章数量最多；故宫内不止一处可买到《紫禁城100》，每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；盖完后可选择邮寄到家或自行携带。
-- **盖章体验**：坤宁宫东北角文创店有5枚免费印章；储秀宫边文创店有3枚免费印章；冰窖书吧有3枚免费印章，盖章时有批折子的感觉；珍宝馆出口商店有3枚免费印章；神武门出口左手边角楼咖啡有2枚免费印章，故宫文创也有2枚免费印章。
-- **打卡体验**：断虹桥是网红打卡地，桥上有形态各异的石狮子，其中最有名的是「武当狮」，可自行寻找；东筒子夹道拍照非常出片，是很多游客喜欢来的地方；慈宁宫旁寿康宫是甄嬛居住地，喜欢《甄嬛传》的游客可到此打卡。
-- **文创体验**：箭亭旁商店可购买文创雪糕，主讲人邀请观众在评论区分享雪糕造型对应的历史人物；冰窖书吧购买了冰溪图。
-- **参观感受**：珍宝馆虽名为馆，但并非单独展厅，院子周围屋子均可参观，每件展品都令人惊叹；馆内游客非常多，尤其看凤冠需挤进去；乐寿堂是故宫内唯一能进去参观的皇家寝室，内有二龙戏珠设计，令人联想到恭王府和珅的卧室。
-- **参观感受**：武英殿陶瓷馆目前关闭，只能在门口看看；文华殿当时未开放，据说现有一个展览可参观。
+- **盖章体验**：保和殿东北角汉字馆有4枚免费印章，可现场购买《紫禁城100》并盖章，工作人员现场操作，主讲人形容「盖了帽了」，并调侃乾隆喜欢盖章；故宫不止一处可买《紫禁城100》，每家店印章不同，购买后不能去其他店铺盖章，需有所取舍，据称汉字馆印章数量最多，盖完可选择邮寄到家或自行携带。
+- **盖章体验**：坤宁宫东北角文创店有5枚免费印章，主讲人提醒别错过。
+- **盖章体验**：储秀宫边文创店有3枚免费印章。
+- **盖章体验**：冰窖书吧有3枚免费印章，主讲人表示盖章时有「批折子的感觉」，并称来之前看过网友分享，认为印章造型好看，在此购买了冰溪图。
+- **盖章体验**：珍宝馆出口商店有3枚免费印章，主讲人提醒喜欢收集印章的别漏掉。
+- **盖章体验**：神武门出门左手边角楼咖啡有2枚免费印章，故宫文创也有2枚免费印章。
+- **拍照互动**：太和门门口铜狮子是故宫六对铜狮中最大的一对，不少人想合影，主讲人建议打消念头，因狮子脚踩寰宇象征权力，站在底下大爪子会盖在头上，单独拍张照即可。
+- **拍照互动**：乾清宫门口摆放铜鹤与铜龟，不少人对着拍照，主讲人提示旁边还有两个精致小房子，即社稷江山金殿，是紫禁城里最小的宫殿。
+- **打卡互动**：慈宁宫旁是寿康宫，主讲人提醒喜欢看《甄嬛传》的游客别忘了到此打卡。
+- **打卡互动**：断虹桥是网红打卡地，桥上有形态各异的石狮子，最有名的是「武当狮」，主讲人邀请游客找一找它在哪。
+- **打卡互动**：东筒子夹道是很多小姐姐喜欢来的拍照地点，主讲人称拍照非常出片。
+- **打卡互动**：延禧宫是网红打卡地，旁边是景仁宫，当年甄嬛被封熹妃时居住，珍妃也住过。
+- **文创体验**：箭亭旁商店可买到文创雪糕，主讲人提问雪糕造型是谁，欢迎在评论区分享。
+- **参观体验**：珍宝馆虽名为馆但不是单独展厅，院子周围屋子都可进入参观，宝贝每样都令人惊叹；但游客太多，尤其看凤冠需「没点技术还真挤不进去」。
+- **参观体验**：乐寿堂是故宫里唯一能进去参观的皇家寝室，内有二层仙楼设计，主讲人提示瞬间想到恭王府和珅的卧室。
+- **参观体验**：珍妃井现上方放的是井口石，珍妃并非从那个小眼进去的。
+- **参观体验**：武英殿现改为陶瓷馆，目前处于关闭状态，只能在门口看看；文华殿主讲人去时未开，据说现有一个展览，感兴趣可去看。
+- **个人感受**：钟表馆的钟表造型令主讲人「开了眼」，感叹故宫宝贝不止这些。
 # 收获与建议
-## 游览路线与时间安排
-- **第一条路线（全天深度游）**：走完视频内提到的所有景点，早起排队一进门就沿中轴线往后走，适合打算在故宫待上一整天的游客；主讲人实测一天走3万步，提醒游览过程中适当休息和补充水分。
-- **第二条路线（半天游）**：进门沿中轴线往后走，看完坤宁宫后去景仁宫和延禧宫，紧接着逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天时间逛完。
-- **第三条路线（省力速览）**：进门沿中轴线往后走，看完坤宁宫后去储秀宫，出来去御花园，然后从神武门出，预计2小时左右逛完，是最省力的路线。
-- **错峰建议**：建议早到排队，进门后先冲中轴线，可错开大批旅游团人群，等大批游客到达时已在人少时逛完最重要的景点。
-## 免费盖章点汇总
-- **保和殿东北角汉字馆**：4枚免费印章，可购买《紫禁城100》由工作人员现场盖章；据称汉字馆印章数量最多。
-- **坤宁宫东北角文创店**：5枚免费印章。
-- **储秀宫边文创店**：3枚免费印章。
-- **冰窖书吧**：3枚免费印章，主讲人评价印章造型好，盖章时有批折子的感觉。
-- **珍宝馆出口商店**：3枚免费印章。
-- **神武门出口角楼咖啡**：2枚免费印章。
-- **神武门出口故宫文创店**：2枚免费印章。
-- **跨店规则提示**：故宫内不止一处可购买《紫禁城100》，每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；盖完后可选择邮寄到家或自行带走。
-## 知识增量与实用信息
-- **午门功能**：明朝皇帝在此杖打犯错大臣，清朝皇帝在此颁发第二年历书（颁朔之礼）；午门三个门洞进门后变五个，即「明三暗五」；中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，旁边两门走皇亲国戚和文武百官。
-- **太和门与太和殿**：太和门是明朝皇帝御门听政（上朝）的地方，门口铜狮为故宫六对铜狮中最大一对，脚踩寰宇象征权力；太和殿是举行盛大典礼（皇帝登基、皇后册封）的场所，并非上朝之地，文武百官在太和殿广场朝拜，站位为「文东武西」。
-- **中和殿与保和殿**：中和殿是盛大典礼时皇帝的休息室；保和殿从乾隆五十四年起为殿试考场。
-- **乾清门与乾清宫**：乾清门是皇帝上早朝的地方，东边九卿直房为等级高的大臣等待召见处，西边为军机处；门口铜狮耳朵耷拉、眉毛遮眼，警示后宫之人「不该看的别看，不该听的别听」；乾清宫为皇帝寝宫，据说有27张龙床以防刺客，「正大光明」牌匾后藏立储诏书，皇帝驾崩后与另一份诏书比对以防篡改。
+## 历史知识与文化认知
+- **午门功能**：明朝皇帝在此杖打犯错大臣，清朝皇帝在此颁发第二年历书（颁朔之礼）；午门为“明三暗五”结构，中间正门仅供皇帝行走，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，旁门走皇亲国戚和文武百官。
+- **太和门与太和殿**：太和门是明朝御门听政（上朝）的地方；太和殿是举行盛大典礼的场所（皇帝登基、皇后册封），并非上朝之地，文武百官在太和殿广场向皇帝行礼，站位为“文东武西”。
+- **中和殿与保和殿**：中和殿是盛大典礼时皇帝的休息室；保和殿从乾隆五十四年开始作为殿试考场。
+- **乾清宫与立储制度**：乾清宫是皇帝寝宫，内有27张龙床（据说是为防止刺客找到皇帝位置）；“正大光明”牌匾后藏立储诏书，皇帝写两份诏书，驾崩后对比验证是否被动过手脚。
 - **坤宁宫与交泰殿**：坤宁宫为皇后住所，明朝所有皇后都住于此；交泰殿内放有25块传国玉玺。
-- **储秀宫与慈宁宫区域**：储秀宫为慈禧住了20多年的地方，现为慈禧五十大寿原状陈列，慈禧因儿子在此出生而偏爱此处；慈宁宫是康熙为奶奶孝庄皇太后修建的养老院，寿康宫为甄嬛（剧中人物）居住地。
-- **珍宝馆与宁寿全宫**：珍宝馆实为宁寿全宫，是乾隆给自己修建的养老院，乾隆退休后未放权仍照常上朝办公；皇极殿据称1:1复刻乾清宫，宁寿宫对标坤宁宫；乐寿堂是故宫内唯一能进去参观的皇家寝室，有二龙仙楼设计；珍妃井现放井口石，珍妃并非从该小眼进入。
-- **九龙壁细节**：珍宝馆门口为我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据传因当年烧制琉璃砖瓦时弄坏一块，工匠为保命用木头刷白漆以假乱真。
-- **其他景点知识**：断虹桥石狮子中「武当狮」最有名；武英殿改为陶瓷馆但目前关闭；文华殿据称有展览；箭亭为清朝皇帝及子孙练习骑马射箭处；御花园钦安殿供奉真武大帝，与景山酷似闭目盘坐人像的造型相呼应；东筒子夹道拍照出片，延禧宫为网红打卡地，景仁宫为甄嬛被封熹妃时所住、珍妃也曾居住。
-- **文创推荐**：箭亭旁商店可购买文创雪糕；冰窖书吧可购买冰溪图。</t>
+- **储秀宫与慈禧**：慈禧在此居住20多年，其子在此出生；现为慈禧五十大寿时期的原状陈列。
+- **慈宁宫与寿康宫**：慈宁宫是康熙为奶奶孝庄皇太后修建的养老院；寿康宫为甄嬛（历史人物）居住地。
+- **珍宝馆与宁寿全宫**：珍宝馆实为宁寿全宫，是乾隆给自己修建的养老院，乾隆退休后未放权、每天照常上朝办公；皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫。
+- **乐寿堂与珍妃井**：乐寿堂是故宫里唯一能进去参观的皇家寝室，有二龙仙楼设计；珍妃井为当年慈禧把珍妃丢进去的地方，井口石为后放，珍妃并非从那个小眼进去。
+- **九龙壁细节**：珍宝馆门口九龙壁为我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据说是当年烧制琉璃砖瓦时弄坏一块，工匠为保命用木头刷白漆以假乱真。
+- **断虹桥与武当狮**：断虹桥上有形态各异的石狮子，最有名的是“武当狮”。
+- **箭亭与钟表馆**：箭亭是清朝皇帝及子孙练习骑马射箭的地方；钟表馆展示清代钟表造型。
+- **御花园与钦安殿**：御花园内钦安殿供奉真武大帝；紫禁城靠山景山从天上看酷似闭目盘坐的人像，有人说该造型就是真武大帝。
+- **其他建筑功能**：弘义阁是皇帝银库（内库），体仁阁是缎库；乾清门东边九卿直房是等级高的大臣等待召见之处，西边为军机处；乾清门门口狮子耳朵耷拉、眉毛遮眼，意在警示后宫之人“不该看的别看，不该听的别听”；社稷江山金殿是紫禁城里最小的宫殿，设于此提醒皇帝把江山社稷（百姓吃饭、民生问题）放在第一位。
+## 游览建议与路线
+- **拍照建议**：太和门门口铜狮子是故宫六对铜狮中最大的一对，建议单独拍照即可，不要站在狮子底下合影，因为大爪子会盖在头上。
+- **第一条路线（全天）**：走完视频内提到的所有景点，适合打算在故宫待一整天的游客；建议早起排队，进门后沿中轴线往后走，可错开大批旅游团人群，一天约走3万步，游览中注意适当休息和补充水分。
+- **第二条路线（半天）**：进门沿中轴线往后走，看完坤宁宫后去看景仁宫和延禧宫，接着逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天时间逛完。
+- **第三条路线（约2小时）**：进门沿中轴线往后走，看完坤宁宫后去储秀宫，出来去御花园，从神武门出，最省力，预计2小时左右逛完。
+- **延禧宫与景仁宫**：延禧宫为网红打卡地；景仁宫是当年甄嬛被封为熹妃时所住，珍妃也住过此地。
+- **东筒子夹道**：拍照非常出片，很多游客喜欢来此打卡。
+- **陶瓷馆状态**：武英殿改为陶瓷馆，目前处于关闭状态，只能在门口看看；文华殿据称有展览，可前往参观。
+## 盖章与文创
+- **盖章点汇总**：故宫内共有七个免费盖章位置——保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫边文创店3枚、冰窖书吧3枚、珍宝馆出口商店3枚、神武门出门左手边角楼咖啡2枚、故宫文创2枚。
+- **紫禁城100购买规则**：故宫不止一处可购买紫禁城100，每家店印章不同；购买后不能去其他店铺盖章，需有所取舍；汉字馆印章数量据说是最多的，盖完后可选择邮寄到家或自行带走。
+- **冰窖书吧体验**：印章造型好，盖章时有“批折子”的感觉；主讲人因已购买紫禁城100，在此购买了冰溪图。
+- **文创雪糕**：箭亭旁边商店可购买文创雪糕。</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>39.3</v>
+        <v>43.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4497/3901</t>
+          <t>4497/4652</t>
         </is>
       </c>
     </row>
@@ -7321,65 +7277,69 @@
       <c r="C21" t="inlineStr">
         <is>
           <t># 访谈概况
-本次访谈围绕留守老人养老问题展开，由记者实地走访农村与城市社区，访谈对象包括村干部、民政局干部、村民及社区社工。访谈目的是了解留守老人养老现状、农村养老政策执行情况及城市社区养老经验，并探讨解决路径。核心议题涵盖独居老人生活困境、农村五保户与养老金政策、社区志愿者帮扶机制及社工制度困境。整体反馈基调以问题揭示为主：农村养老存在经济困难、子女不在身边、娱乐方式少等痛点，城市社区虽有志愿者与养老服务中心等探索，但社工行业面临工资低、人员流失、资金不足等现实制约。
+本次访谈围绕留守老人养老问题展开，通过农村与城市双线对比，探讨养老现状、政策落实、社工困境及社区志愿者模式。访谈对象包括村政府与民政局干部、农村留守老人、城市社区社工及志愿者，由主持人实地走访采集。核心议题涵盖独居老人生活困境、农村养老补贴与设施运营、城市社区帮扶机制及社工行业供给不足。整体反馈基调以问题揭示为主：农村方面突出经济困难、子女缺位与设施经费断档，城市方面则呈现志愿者激励有效但专业社工缺口大、项目资金不稳定等矛盾。据2021年报告数据，65.5%的老人子女长期不在身边，仅有26.8%与子女同住；农村2021年公安数据显示约17.8%老人为空巢，老龄化程度预计加剧。
 # 核心反馈
-## 村干部（发言人2）
-- **独居规模**：据公安数据，2021年当地73万多老人中约17.8%为独居，且因1962—1965年职工档案出生人口集中、去年开始退休，老龄化程度预计还会加重。
-- **经济困难**：当地经济不发达，老人生病、锻炼等首要问题是经济困难。
-- **子女不在身边**：老人一旦生病住院比较麻烦，缺乏亲人陪伴。
-- **娱乐方式少**：老人只能坐在一起聊天、打牌。
-- **养老设施运营断档**：此前探索在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但“不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的”。
-- **五保户供养**：集中供养的五保户，生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养的五保户每月发475元生活费，另有护理补贴。
-- **政策建议**：请专业施工人进行陪伴；倡导在外务工子女多联系老人；丰富文化生活、增加娱乐方式；希望老年协会专项执行、专门建养老设施，有固定场地，定期开展板报宣传或健康知识讲座，并保障持续运营经费。
-## 民政局干部（发言人4）
-- **五保户补贴**：每月补贴加食补电补共600来块钱，农村生活艰苦，五六百元基本能满足，但“如果你要大吃大喝也不行”。
-- **残疾人保障**：一级二级残疾人按国家政策纳入最低生活保障，有160、270、380元三个标准，视家庭状况制定，至少保证最低生活保障。
-- **走访帮扶**：靠村支两委和志愿者“敲门串门”、宣传政策、搞卫生；每月开一次党员组织会，上午开会、下午搞活动或大扫除，到孤寡老人、留守老人家里走一圈。
-- **上门服务不足**：所有上门服务都入户签约的只有一个，有的一个都没有。
-- **养老金不公**：60岁以上农村老年人每月118元养老金，还需提高；农村老人“结个婚砍个树都要交砍伐金，杀个猪都要交屠宰税”，农村养老金与工人养老金待遇完全一样才公平。
-## 村民（发言人5、6、7）
-- **子女外出**：村里80%年轻人都外出打工，老人无人照看。
-- **独居孤独**：老人独自在家，想找人说话都难，有人敲门不开、无人亲近。
-- **日常劳作**：老人仍要喂鱼、喂猪、养七八个猪，忙个不停。
-## 社工（发言人8）
-- **志愿者一对一帮扶**：社区给志愿者划分一对一帮扶对象，志愿者发现老人住自家楼下，上下楼就天天去看，老人身体不好时天天送菜。
-- **志愿者激励**：定期表彰、志愿者积分兑换，年底可到雷锋超市兑换礼品，让志愿者长期坚持。
-- **小手拉大手**：今年从儿童青少年入手，让孩子拉动家长加入志愿者队伍。
-- **送春联活动**：这周四准备开展送春联活动，邀请书法老师写对联，孩子上门给老人送。
-- **节日活动**：去年中秋节开展做月饼活动，还做过百家宴，让老人感觉社区就是大家庭。
-- **2023年目标**：让家长自己组织活动，社区作为协助者。
-- **养老服务中心**：每个社区都要成立养老服务中心，有理疗类活动。
-- **心理问题老人案例**：一位老人与邻里关系不和谐、半夜摔门，志愿者上门但老人抗拒，“我不需要你的关心”，觉得周围人都是陌生的、没有关心他的人；经长期照料，现在与邻里关系好转、能接受意见，但今天还打来电话说“寂寞空虚，得不到人关注一样的”。
-- **社工工资低**：社工行业迅速发展但工资低，影响就业率，“基本上很多同学就没做多久，基本上都垮了，可能不超过一年”。
-- **驻点社工难持续**：每个街道和乡镇派两名社工驻点，围绕老人小孩服务，但“说实在话也很难能够走下来”。
-- **项目资金断档**：社工服务需花钱购买，不一定今年服务了明年还能服务，要看领导能否争取到项目；一年服务成效不明显，资金拨不下来项目就结束，服务成效不一定达到。
-- **社工专业性欠缺**：湖南省街道社工服务要花十来万块钱，省里拨了钱，但很多社工并非社工专业出身，“可能也就是图一个，周末玩玩”，专业上很欠缺。
+## 农村留守老人
+- **独居普遍**：据2021年社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住；独居老人不同程度存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自在家发生意外。
+- **孤独求助案例**：黑龙江绥滨一位独居老奶奶报警称有人敲门，民警上门调查后老奶奶承认是因独自在家太寂寞、想找人聊天才报警。
+- **独居死亡未被及时发现**：上海一名67岁独居老人在家中去世，多日后家中溢出刺鼻气味才被邻居发现；杭州一小区67岁独居老人同样去世数天后才被发现。
+- **子女外出务工导致留守**：农村老人反映“现在80%都是都提醒这个在外面做这些事的，年轻人都卖出去了”，子女外出打工、老人独自留守是普遍现象。
+- **经济困难**：村政府/民政局干部指出留守老人问题第一是经济困难，“我们这个地方经济不太发达嘛”，生病、锻炼等都受经济条件制约。
+- **子女不在身边、生病住院麻烦**：干部指出“子女不在身边，一旦生病住院啊就比较麻烦”。
+- **娱乐方式少**：老人娱乐方式少，“就坐在一起聊聊天啊，打打牌呀”。
+- **养老设施运营经费无后续支持**：此前探索在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，“但是不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的”。
+- **养老金水平偏低**：农村60岁以上老人每月养老金118元，加上食补电补共600来块钱；干部认为“农村的养老金跟工人的养老金待遇完全一样，但现在的老年人公平”，并指出“毕竟都是60年代的人了，结个婚呢砍个树都要交砍伐金，杀个猪都要交那个屠宰税”。
+- **五保户供养标准**：分散供养的五保户每月发475元生活费，另有护理补贴；集中供养的将生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院。
+- **残疾人低保标准**：一级二级残疾人按国家政策纳入最低生活保障，有160、270、380元三个标准，视家庭状况制定。
+- **老龄化程度预计加剧**：据公安数据，2021年当地73万多老人中约17.8%为空巢，“因为我说662年到65年那个职工档案出生的人特别多，那年去年开始退休了，所以过了几年肯定就是老龄化程度会越来越严重”。
+## 城市社区留守老人与社工
+- **城市留守老人社交机会更少**：与农村相比，城市小区留守老人与外界社交机会更少，更容易产生孤独、抑郁等情绪。
+- **心理问题个案**：社工曾帮助一位存在心理问题的老人，该老人与邻里关系处理不和谐、半夜摔门，志愿者上门时出现抗拒，“我不需要你的关心”，觉得周围人都是陌生的、没有关心他的人；经长期关心照料后与邻里关系好转、能接受意见，但老人仍打电话说“寂寞空虚，得不到人关注一样的”。
+- **社工供给不足**：社工制度困境主要在于社会需求量大而供给不足，政府和社区资金有限，难以承担长期专业社工服务费用。
+- **社工工资低、流失率高**：社工行业迅速发展但工资较低，影响就业率，“基本上很多同学就没做多久，基本上都垮了，可能不超过一年”。
+- **社工服务项目资金不稳定**：社工服务需要花钱购买，项目资金拨不下来就结束，“一年的服务成效并不是那么的明显”，“今年服务了，明年又能服务”不一定，要看领导能否争取到项目。
+- **社工专业性欠缺**：湖南省每个街道社工服务要花十来万块钱，省里拨了钱，但“很多的社工并不是专业的，学社工专业出来的。可能也就是图一个，周末玩玩。在专业上其实还是很欠缺的”。
+- **社工服务领域分散**：长沙社工机构服务领域多，同一社工可能这次做留守儿童、下次做留守老人，“专注力可能也不在一个点了”。
 # 关键洞察与建议
-## 农村养老政策执行困境
-- **运营经费断档**：村干部指出此前探索在农村建设养老公共设施、提供日托和休闲娱乐场地，但地方财政困难，一次性投入后运营经费无后续支持，设施难以持续发挥作用。
-- **养老金待遇不公**：民政局干部反映60岁以上农村老年人每月养老金118元，认为应提高；农村养老金与工人养老金待遇完全不同，而老一辈农村老人当年结婚、砍树、杀猪都要交费，如今待遇却不对等，有失公平。
-- **五保户供养方式**：村干部介绍五保户分集中供养和分散供养两种——集中供养将生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养每月发475元生活费加护理补贴，民政局干部补充加上食补电补共600来块钱，基本能满足农村生活但无法大吃大喝。
-- **残疾人保障分级**：民政局干部说明一级二级残疾人按国家政策纳入最低生活保障，分160、270、380元三档，按家庭状况制定标准，至少保证最低生活保障。
-- **老龄化趋势加剧**：村干部根据公安数据判断，1962至1965年职工档案出生人口多、去年开始退休，未来几年老龄化程度会越来越严重。
-## 城市社区养老经验与社工困境
-- **志愿者激励与传承**：社工介绍社区为志愿者划分一对一帮扶对象，志愿者可定期获表彰或积分兑换，年底到雷锋超市兑换礼品；今年开展"小手拉大手"活动，从儿童青少年入手拉动家长加入志愿者队伍。
-- **社区活动增进归属**：社工提到这周四准备开展送春联活动，邀请书法老师写对联、孩子上门送给老人；去年中秋节开展做月饼活动，还办过百家宴，让老人感受社区大家庭氛围。
-- **活动组织权转移**：社工提出2023年目标是让家长自己组织活动，社区转为协助者角色，改变此前每次活动都由社区策划开展的模式。
-- **社工供给不足**：社工反映每个街道和乡镇派两名社工驻点，围绕老人小孩服务但很难持续；社工行业工资低影响就业率，很多同学做不超过一年就离职。
-- **项目资金不稳定**：社工说明社工服务需花钱购买，项目能否延续取决于领导能否争取到，湖南省一个街道服务要花十来万块钱，省里虽拨了钱但资金拨不下来项目就结束，一年服务成效不一定达到。
-- **专业能力欠缺**：社工指出很多从业者并非社工专业出身，专业上很欠缺，可能只是图周末玩玩。
-## 受访者提出的建议
-- **村干部提出四项建议**：请专业施工人员进行陪伴；倡导在外务工子女多与老人联系；丰富老人文化生活、增加娱乐方式；希望老年协会专项执行、专门建养老设施，有固定场地定期开展板报宣传或健康知识讲座，并给予持续运营经费。
-- **民政局干部建议提高农村养老金**：认为60岁以上农村老年人每月118元养老金应提高，以体现与工人养老金的公平。
-- **社工建议发掘中年志愿者**：在原有志愿者基础上发掘一批偏中年一点的志愿者，以保障志愿服务的长期持续。</t>
+## 农村养老困境的深层判断
+- **事实**：发言人2指出当地经济不发达，老人面临经济困难、子女不在身边导致生病住院麻烦、娱乐方式少三大问题。
+- **判断**：农村养老困境是经济、照料、精神慰藉三重缺失叠加的结果，单一政策难以覆盖全部需求。
+- **事实**：发言人2提到此前探索过在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续没有支持。
+- **判断**：农村养老设施「建得起、养不起」是普遍瓶颈，一次性投入不等于可持续服务。
+- **事实**：发言人4介绍农村老人每月养老金118元，加上食补电补共600来块钱，并指出农村养老金与工人养老金待遇完全不一样，但老年人年轻时结婚砍树要交砍伐金、杀猪要交屠宰税。
+- **判断**：受访者认为农村老人历史贡献未被充分纳入养老待遇核算，存在公平性诉求。
+- **事实**：发言人2从公安数据判断，1962至1965年职工档案出生的人特别多、去年开始退休，老龄化程度会越来越严重。
+- **判断**：未来几年农村空巢老人规模将持续扩大，养老压力有加速趋势。
+## 受访者提出的改善建议
+- **专业陪伴**：发言人2建议请专业的施工人员进行陪伴。
+- **子女联系**：发言人2建议倡导在外务工的子女多与老人联系。
+- **丰富文化生活**：发言人2建议丰富老人的文化生活，增加更多娱乐方式。
+- **老年协会专项执行**：发言人2希望老年协会专项执行，专门建养老设施，有固定场地，定期开展板报宣传或健康知识讲座。
+- **持续运营经费**：发言人2强调不仅要考虑建设，还要考虑后续持续运营经费，才能更好发挥作用。
+## 城市社区模式的启示
+- **事实**：社区建立志愿者一对一帮扶制度，志愿者发现老人住在楼下就天天去看望，身体不好时天天送菜；通过定期表彰和志愿者积分兑换（如雷锋超市）维持志愿者积极性。
+- **判断**：就近帮扶加物质与荣誉双重激励，是维持志愿服务可持续性的有效机制。
+- **事实**：社区开展「小手拉大手」活动，从儿童青少年入手拉动家长加入志愿者队伍；今年计划开展送春联活动，让孩子上门给老人送对联。
+- **判断**：以代际参与为切入点，可扩大志愿者来源并增强社区凝聚力。
+- **事实**：去年中秋节开展做月饼活动、还做过百家宴；2023年目标是家长自己组织活动，社区转为协助者角色。
+- **判断**：社区活动正从社工主导转向居民自治，有助于降低对有限社工资源的依赖。
+- **事实**：社工姐姐曾帮助一位心理问题严重的老人，该老人与邻里关系不和谐、半夜摔门、抗拒外界关心，经日复一日关心照料后心理问题逐渐好转，能接受他人意见。
+- **判断**：对心理封闭的独居老人，持续上门关怀比一次性服务更有效，但需要足够耐心与时间投入。
+## 社工制度困境的改进方向
+- **事实**：社工工资低影响就业率，很多同学做不超过一年就离职；湖南省一个街道社工服务要花十来万块钱，项目资金拨不下来、项目结束但服务成效不一定达到。
+- **判断**：资金不稳定与待遇偏低直接导致社工流失，制约服务连续性，项目制采购难以保障长期成效。
+- **事实**：很多社工并非社工专业出身，专业能力欠缺；社工服务领域分散（这次做留守儿童、下次做留守老人），专注力不集中。
+- **判断**：专业化不足与领域分散并存，需要提升从业者专业水平并稳定服务方向。
+- **事实**：发言人8提到每个街道和乡镇派两名社工驻点，围绕老人、小孩服务，但「很难能够走下来」。
+- **判断**：驻点社工覆盖面有限，难以应对庞大的服务需求，需探索更高效的资源配置方式。</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>44.2</v>
+        <v>42.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5309/3125</t>
+          <t>5309/3397</t>
         </is>
       </c>
     </row>
@@ -7986,87 +7946,90 @@
       <c r="C22" t="inlineStr">
         <is>
           <t># 沟通概况
-班主任林瑞在372班家长会上向家长介绍班级情况与家校协同事项。班级共60人，男生25人、女生35人，学生处于生理心理持续变化的初中阶段；整体时间观念与执行力强、班风班貌纪律良好，但少数同学存在周末玩手机游戏、思考能力差、自习课纪律差等问题。教师团队多为老教师、优秀教师，班主任林瑞任教地理学科。针对班级问题，林瑞提出解决思路：个别学生书写差已与家长沟通并建议练字；自习课效率低需加强班委培训；手机管理要求上交并请家长不定时电话检查；关注网瘾、不健康直播及谈恋爱现象。班级管理计划包括每日思想教育、制定严格班规、严格请假制度、定期家校沟通，下次月考在11月初。林瑞指出家长常见误区并给出建议，家长代表张宇波分享家庭教育经验。会议还涉及成立家长委员会（至少三人自愿）、保险购买（约310元）、电子学生证办理（套餐78元）及资助政策说明。
+班主任林瑞在372班家长会上，围绕班级基本情况、教师团队、存在问题及解决思路、计划与措施、给家长的建议等板块与家长沟通。班级共60人（男生25人、女生35人），整体班风纪律良好，但存在少数学生周末玩手机、自习课效率低、个别书写不良等问题。林瑞提出加强手机管理（上交手机、家长不定时电话检查）、制定详细班规、严格请假制度等举措，并建议家长关注学生心理健康与社交账号，注意交通、防溺水等安全教育。家长代表张宇波分享家庭教育经验，强调先做人再学习、尊重孩子、多倾听交流。会议还议定成立家长委员会（至少三人自愿参加）、家长为孩子购买保险（约310多元）、办理电子学生证（套餐78元）等事项。
 # 沟通内容
-## 亮点
-- **时间观念与执行力**：整体来看第一个月，学生时间观念、执行力加强，班风班貌纪律良好，周边环境地面干干净净，卫生状况良好。
-- **主动请教意识**：学生遇到问题会积极上来问老师，会主动向老师汇报，非常关注学习。
-## 需关注之处
-- **周末玩手机游戏**：少数同学主要在周末了解和爽一玩游戏，玩累了、玩过了，显得懒散，有两三个学生手机使用过度（原文如此）。
-- **自习课纪律差**：思考能力比较差，班主任在的时候学生很乖，班主任不在就乱哄哄的；需加强人员管理和班委培训。
-- **书写问题**：个别学生书写差，已与家长说了，建议家长看学生手册后买字帖练字；有学生把班计划372班写成172班（原文如此）。
-- **手机管理**：目前玩手机现象未发现（原文如此），要求手机上交，专门放手机箱，每个名字贴好；有学生有两个手机，家长家里可能有五个手机，家长要处理掉多余的，不要留多的。
-- **网瘾问题**：发现少数男生有网瘾，星期六晚上有学生充生活费充了400元（原文如此），有学生观看不健康直播内容。
-- **谈恋爱现象**：需多关注学生谈恋爱，尤其是QQ、空间朋友圈、抖音、快手等社交账号，有学生可能把家长屏蔽了。
-- **阅读不良小说**：家里有的小说要管理，两个店让他看（原文如此），知道目标后把他叫出去看了（原文如此）。
-- **零花钱使用不当**：少数学生生活费不是用于学习和就业，而是用于非正常消费；有男生出去过生日，喝了酒回来一身酒气还抽烟、玩手机。
-- **安全意识**：未满16周岁骑电动车非常危险，有学生会载两个载三个；需注意交通安全、运动安全、饮食安全、防诈骗、防溺水、防校园欺凌。
+## 班级整体表现
+- **亮点**：时间观念执行力加强，班风班貌纪律良好，地面干净、卫生好
+- **亮点**：班风班貌纪律非常好，周边环境能感受到
+- **需关注**：少数同学周末玩手机游戏，玩累了之后懒散，有少数两三个同学手机依赖（原文如此）
+- **需关注**：思考能力比较差，自习课时班主任在就乖，不在就乱哄哄
+- **需关注**：个别学生书写不良，班主任已与个别家长说过，建议家长看学生手册后买字帖练字
+- **需关注**：自习课效率比较低
+## 手机与网络管理
+- **需关注**：有少数男生有网瘾，打游戏，星期六晚上有学生充生活费充了400元（原文如此）
+- **需关注**：发现班上有男生观看不健康直播内容（原文如此）
+- **需关注**：有同学带手机，要求上交，专门一个手机存放箱，每个名字贴好
+- **需关注**：有学生可能有两个手机，家长家里可能有五个手机，建议家长处理掉多余的，不要留多
+- **需关注**：家长可在周一到周五不定时打电话检查，如果电话能打通没人接，说明手机有问题；如果打过去关机，说明已上交
+- **需关注**：昨天在抽屉里发现有同学拿镜子，大概10个人（原文如此），希望家长也检查孩子书包
+## 行为与社交
+- **需关注**：谈恋爱问题，建议家长加孩子QQ，关注其空间朋友圈，注意是否被屏蔽
+- **需关注**：建议家长关注孩子抖音、快手账号，可能有3个账号（原文如此），看不出有没有谈恋爱
+- **需关注**：有学生看小说，建议家长管好
+- **需关注**：有学生过生日出去喝酒回来一身酒气还抽烟，周六选择住校的话要遵守纪律要求
+- **需关注**：有学生生活费使用不当，一个星期说买回去又买回去，结果跑到家里面（原文如此），据了解该同学当时是因为手机问题被老师说了
+## 学习与目标
+- **亮点**：学生手册记录良好，可以看到学生的学习情况、作业情况
+- **需关注**：个别学生把班计划372班写成172班，书写太差（原文如此）
+- **计划**：学生手册中已定月考目标，下次月考在11月初
+- **计划**：班主任每天加强思想教育，制定详细班规，该扣分扣分、该写检讨写检讨、该罚站罚站
+- **计划**：严格请假制度，稳定学习秩序
+- **计划**：班主任定期与科任老师沟通，了解学生表现
+- **计划**：各科老师认真备课、用心上课、关爱每一位学生
 # 家长反馈
 ## 家长关注的问题与诉求
-- **手机管理**：班主任要求家长配合检查学生手机是否上交，可不定时打电话验证手机是否开机或有人接听，发现未交需处理；家长需清理家中多余手机，避免学生藏匿备用机。
-  - 班主任建议家长周一到周五不定时打电话检查，若电话能打通但无人接听，说明手机可能未上交。
-  - 班主任提醒家长关注学生手机中的内容，曾发现学生观看不健康直播，建议家长检查手机应用、QQ空间、朋友圈、抖音、快手等账号。
-- **生活费与消费**：班主任提醒家长控制零花钱额度，建议每周生活费不超过150元（按每天21–24元标准计算），避免学生将钱用于买手机、玩游戏、过生日聚会等非正常消费。
-  - 班主任举例：有学生一周内多次以买学习用品为由向家里要钱，实际用于其他用途；有男生外出过生日喝酒、抽烟，违反住校纪律。
-- **学生安全**：班主任提醒未满16周岁骑电动车非常危险，尤其载两三个同学；要求家长提醒孩子注意交通安全、运动安全、饮食安全、防诈骗、防溺水，发现异常第一时间联系班主任。
-- **心理健康与情感**：班主任建议家长关注学生心理动态，多沟通、多鼓励、少批评；关注学生是否谈恋爱，建议家长查看学生QQ、抖音、快手等社交账号是否有异常。
-- **学习习惯**：班主任指出个别学生书写差，已与家长沟通，建议家长购买字帖让孩子练字；自习课效率低，需加强管理。
-- **电子学生证办理**：班主任说明班级目前仅有两个老年机可用、一个已停机，建议家长办理电子学生证（移动套餐78元），方便联系学生；能办的就办，不能办的说明情况。
-- **保险购买**：班主任说明保险费用约310元，家长可自行购买（校内、校外、阿里巴巴平台均可），需统计购买情况，为学生提供保障。
-- **资助政策**：班主任提醒高中阶段补助打在学生医保卡上，家长需关注到账金额及用途，避免学生将补助用于不当消费。
+- **家长代表分享家庭教育经验**：家长代表张宇波（校长代表）在家长会上分享家庭教育心得，强调家长要控制孩子的身体健康和心理健康，教育孩子先做人再学习，家长要有平常心帮助孩子面对挫折和失败，尊重孩子、给孩子自由空间，不轻易下消极评价，多倾听多交流，配合学校制度、尊重老师。
+- **家长自愿参加家委会**：班主任提议成立家长委员会，建议至少需要三人，有家长自愿参加，家委会事项需经班主任和家长探讨。
 ## 家长原话
 &gt; “无论怎样，那你都是爸爸妈妈心里最优秀的儿子，你先批评他，还是不当，这样的话他会更加的深刻，这样的话更加的深刻。”
-- 背景：家长代表张宇波在家长会上分享家庭教育经验时，讲述自己如何安慰考试失利的孩子，强调先肯定孩子再指出问题。
+- 背景：家长代表张宇波在家长会上分享自己与儿子关于批评与鼓励的对话，针对如何正确对待孩子犯错的问题。
 &gt; “要想让孩子离开，就要让他们学会怎么样做人，千万不能让他们带上不良的风气。”
-- 背景：家长代表张宇波在家长会上分享教育理念，强调教育孩子先做人、再学习。
+- 背景：家长代表张宇波在家长会上分享家庭教育经验，强调教育孩子先做人再学习。
 # 共识与配合事项
 ## 手机与网络管理
-- [ ] **家长**：配合执行手机上交制度，学生到校后手机放入贴有姓名的手机存放箱，发现未交需处理
-- [ ] **家长**：周一到周五不定时拨打学生电话检查，若电话能打通但无人接听，说明手机未上交，需及时处理
-- [ ] **家长**：家中多余手机（含备用机、旧机）处理掉或收好，避免学生拿旧手机应付上交、留好手机自用
-- [ ] **家长**：检查学生手机内容，关注是否安装游戏、观看不健康直播或浏览不良内容
-- [ ] **家长**：关注学生QQ、抖音、快手等社交账号，留意是否有谈恋爱迹象或异常动态（如被屏蔽需注意）
-- [ ] **班主任**：继续加强手机管理，发现学生玩手机及时处理
-- [ ] **班主任**：对少数有网瘾的男生加强关注与引导
-## 学习与行为习惯
-- [ ] **家长**：查看学生手册及作业书写情况，书写差的学生到文具店购买字帖练字
-- [ ] **班主任**：加强自习课管理，加强对班委的培训，提升自习课效率
-- [ ] **班主任**：继续加强思想教育工作，每天进行
-- [ ] **班主任**：制定详细班规，严格执行扣分、写检讨、罚站等纪律要求
+- [ ] **家长**：配合学校手机管理制度，督促孩子每周一至周五按时上交手机，周末在家也需控制使用时间
+- [ ] **家长**：不定时拨打孩子手机检查是否处于开机状态，若电话能打通但无人接听，说明孩子可能未按要求上交手机
+- [ ] **家长**：清理家中多余手机，只保留一部供孩子使用，避免孩子藏匿多部手机
+- [ ] **家长**：检查孩子手机中的社交账号（`QQ`、`抖音`、`快手`等），关注是否存在网瘾、观看不健康内容或早恋迹象
+- [ ] **班主任**：在班级设置手机存放箱，每个学生姓名贴好标签，统一管理上交手机
+- [ ] **班主任**：对发现的上课玩手机行为按规定处理，发现即收缴
+## 学习与纪律管理
+- [ ] **班主任**：继续每天加强思想教育工作
+- [ ] **班主任**：执行详细班规，该扣分扣分、该写检讨写检讨、该罚站罚站
 - [ ] **班主任**：严格请假制度，稳定学习秩序
-- [ ] **班主任**：定期与家长沟通，了解学生各方面表现
-- [ ] **班主任**：关注学生心理健康，发现异常及时进行心理辅导
-- [ ] **家长**：关注学生心理动态，多沟通、多鼓励、少批评，适当给予压力但期望不宜过高或过低
+- [ ] **班主任**：加强班委培训，提升自习课管理效率，自习课允许学生讨论、可离座请教问题
+- [ ] **班主任**：定期与科任老师沟通，了解学生课堂表现和学习情况
+- [ ] **家长**：关注孩子书写质量，根据学生手册中作业情况判断是否需要购买字帖练习书写
+- [ ] **家长**：帮助孩子制定合理的学习目标，参照学生手册中记录的月考目标，下次月考在11月初
+## 安全教育与心理健康
+- [ ] **家长**：提醒孩子注意交通安全，未满16周岁不得骑电动车，尤其禁止载人
+- [ ] **家长**：提醒孩子注意运动安全、饮食安全、防诈骗、防溺水
+- [ ] **家长**：关注孩子心理健康，发现异常及时联系班主任进行心理辅导
+- [ ] **家长**：关注孩子生活费使用情况，合理控制零花钱，避免过度消费
+- [ ] **班主任**：发现校园欺凌等问题第一时间处理，家长遇到孩子异常情况可随时联系
+## 家校沟通与家庭环境
+- [ ] **家长**：创造和睦、祥和、稳定的家庭气氛，多鼓励少批评，不给孩子过多压力
 - [ ] **家长**：避免教育误区——不过分关注、不放任不管、不期望过高、不给过多零花钱
-- [ ] **家长**：给孩子制定容易达到的小目标（如年级排名120–190名范围），激发潜能
-- [ ] **家长**：创造和睦、祥和、稳定的家庭气氛，不在孩子面前长时间玩手机，不聚众打麻将、点外卖，不在家里常备零食
-- [ ] **家长**：多抽时间了解孩子在校表现，孩子犯错时引导而非指责
-## 安全教育
-- [ ] **家长**：提醒孩子注意交通安全，未满16周岁骑电动车非常危险（尤其载人），如实在要骑须单人骑行
-- [ ] **家长**：提醒孩子注意运动安全、饮食安全、防诈骗、防溺水
-- [ ] **家长**：关注防校园欺凌，孩子遇到问题第一时间联系班主任处理
-- [ ] **班主任**：对学生安全问题进行教育提醒
-## 费用与保险
-- [ ] **家长**：保险自愿购买（费用约310元），可在学校购买或自行在菜市场、阿里巴巴等渠道购买，购买后需统计
-- [ ] **班主任**：统计学生保险购买情况
-- [ ] **家长**：建议办理电子学生证（移动套餐78元），方便联系；班级目前仅有两个老年机可用，其中一个已停机，另一个用班主任身份证办理尚未处理
-- [ ] **班主任**：将新的电子学生证号码发到家长群，家长需重新补充登记
-- [ ] **家长**：关注资助政策（已发家长群），高中阶段所有补助打在医保卡上，注意孩子收到补助后的使用情况
-- [ ] **班主任**：每次补助发放时提醒家长注意金额及用途
-## 家委会与后续安排
+- [ ] **家长**：多抽时间了解孩子在校表现，经常与孩子沟通，了解心理动态
+- [ ] **家长**：不在孩子面前长时间玩手机，不聚众打麻将，为孩子创造良好学习环境
+- [ ] **家长**：配合学校制度，尊重老师工作，有教育问题及时与班主任沟通
+## 保险、电子学生证与资助
+- [ ] **家长**：为孩子购买保险，费用约310多元，可在学校购买或自行在`阿里巴巴`等平台购买，购买后需统计上报
+- [ ] **家长**：办理电子学生证，套餐78元（移动套餐），方便与孩子联系及请假管理
+- [ ] **班主任**：统计保险购买情况，汇总未购买名单
+- [ ] **班主任**：将新的电子学生证号码发到家长群，更新联系方式
+- [ ] **家长**：关注高中资助政策，高中补助打在医保卡上，需与孩子确认资金用途，防止乱消费
+## 家委会成立
 - [ ] **家长**：自愿报名参加家长委员会，至少需要三人
-- [ ] **班主任**：家委会事项需经班主任与家长共同探讨后确定
-- [ ] **家长**：下次月考在11月初，关注学生月考目标（已记录在学生手册中）
-- [ ] **家长**：会后如需办理电子学生证等业务，可在3:20–3:30期间前往办理
-- [ ] **家长**：培训期间不得拍照发朋友圈或社交媒体（教官着装不允许拍照）</t>
+- [ ] **班主任**：组织家委会成立事宜，重大事项经班主任与家长探讨后决定</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>55.3</v>
+        <v>54.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17334/3660</t>
+          <t>17334/3151</t>
         </is>
       </c>
     </row>
@@ -8147,49 +8110,47 @@
       <c r="C23" t="inlineStr">
         <is>
           <t># 例会概况
-本次周会于10月28日召开，会议性质为自愿级，主题为总结工作并安排下周任务。会议资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。会议围绕工作方向与任务安排、社区介绍与宣传、待遇与休假等议题展开讨论：工作方向与任务安排方面，当前共有四个任务，其中课程开发为任务之一，下月主要任务为组建执法队伍，任务一第一步是确定路线、修订纲领章程，修订303相关文件已基本完成，组建执法队伍需招聘20多位师傅，该议题部分已定、部分待定；社区介绍与宣传方面，社区介绍文件已修改并将“我们是谁”提到最上面，宣传方式包括抖音任务和公众号，该议题已定；待遇与休假方面，待遇为上班5000元、额外有奖励和提成，休假为周五半天加周末两天，该议题仅同步。整体来看，社区介绍文件修改等事项进展顺利，但工作方向可能偏了、任务工作量需考虑、活动费用未统计。下一步将开始邀请同事加入，并计划线下继续学习。
+本次周会于10月28日召开，会议等级为自愿级，会议资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。会议围绕工作总结、社区建设、任务分配、课程开发、执法队伍组建等议题展开讨论。工作方向与任务安排方面，下周主要任务是组建执法队伍，需组建教育团队、确定路线并修订纲领章程，任务包括课程开发，需招聘20多位师傅，相关讨论尚待进一步细化；社区建设与成员要求方面，强调社区环境重要性，成员按角色分为学生、教师、家长、学校、教育主管，需防止坏人进入，方向已明确；待遇与休假方面，明确上班5000元、额外有奖励和提成，休假为周五半天加周末两天，已定；学习介绍修改方面，已将“我们是谁”提到最上面，公众号和抖音任务已讨论，修改基本完成。整体上学习介绍修改等事项推进顺利，但工作方向可能偏了、工作量需考虑，会议纲要是否还需修改待定。会议结论为下一步邀请同事加入，继续线下学习。
 # 工作进展
-## 社区介绍与宣传
-- **社区介绍文件修改**：已将“我们是谁”部分提到文件最上面，完成初步修改；下一步根据会议讨论继续调整内容与排版。
-- **宣传渠道梳理**：讨论涉及抖音任务与公众号运营，作为社区宣传的主要载体；具体发布计划与内容排期待后续安排。
-## 任务推进
-- **课程开发**：为当前四个任务之一，处于规划阶段；需结合社区定位确定课程方向与内容框架。
-- **组建执法队伍**：下月主要任务，需招聘20多位师傅；任务一第一步为确定路线、修订纲领章程，该步骤启动后即安排任务分工。
-- **修订303相关文件**：已完成一轮修订，基本接近完成；待成员自行查看后确认或打勾。
-## 待遇与休假
-- **待遇方案**：上班月薪5000元，额外有奖励与提成；具体发放与结算方式待月会进一步明确。
-- **休假安排**：周五半天加周末两天；已按此口径讨论，未再调整。
-## 后续行动
-- **邀请同事加入**：社区介绍文件完成后即启动邀请工作；会后先了解有意向人员，再逐一沟通。
-- **线下学习计划**：会议讨论转为线下继续学习，时长约一小时；具体时间与地点待定。
+## 社区建设与学习介绍
+- **学习介绍修改（✅已完成）**：已将“我们是谁”部分提到最前面，并同步调整了封面与镜头衔接；下一步将学习介绍发送给成员审阅，确认后进入邀请同事加入环节。
+- **公众号与抖音任务（🔄进行中）**：已讨论公众号运营与抖音任务的可视化学习方案和工具，涉及服务时间与工具调整；下一步根据数据配热情况确定每月充值赞助方案，具体费用待统计。
+- **社区成员角色划分（🔄进行中）**：已按学生、教师、家长、学校、教育主管五类角色划分社区成员，并明确需防止坏人进入；下一步结合角色定位完善社区环境建设方案。
+## 任务与队伍建设
+- **组建执法队伍（🔄进行中）**：确定为下月主要任务，是当前占比最大的任务，需招聘20多位师傅组建教育班队；下一步确定路线并修订纲领章程，随后安排任务分工。
+- **课程开发（🔄进行中）**：已列为四个任务之一，开发性质待明确；下一步结合教育团队组建推进课程内容设计。
+- **纲领章程修订（🔄进行中）**：已修订303相关章程，基本接近完成；下一步由成员自行审阅后打勾确认。
+- **大运发放调试（🔄进行中）**：工作刚开始，目前仅以志愿者身份参与；下一步继续调试发放流程。
+## 待遇与运营
+- **待遇方案（🔄进行中）**：已明确上班5000元，额外有奖励和提成，休假为周五半天加周末两天；下一步在月会上正式发放薪资待遇。
+- **账单统计（🔄进行中）**：发现两个账单未发送，全场活动的优美和棒棒糖待遇尚未发放，导致今日余额趋势比上次多；下一步完成发放后再入职统计。
 # 决定与待办
-- **会议定性**：本次会议定义为自愿级周会，日期为10月28日，主题为总结工作。
-- **下月主要任务**：组建执法队伍，需招聘20多位师傅，任务一第一步为确定路线、修订纲领章程。
-- **纲领章程修订**：修订303相关文件已基本完成，需成员自行查看并打勾确认。
-- **社区介绍文件**：已修改完成，将“我们是谁”提到最上面。
-- **邀请同事加入**：下一步开始邀请同事加入，会后看有谁愿意参与。
-- **线下学习安排**：计划线下继续学习，时间已超一小时，决定转到线下进行。
+- **下周主要任务**：组建执法队伍，为下月主要任务。
+- **组建教育团队**：需组建教育团队，确定路线并修订纲领章程。
+- **课程开发**：任务包括课程开发，需招聘20多位师傅。
+- **学习介绍修改**：已将“我们是谁”提到最上面，修改完成。
+- **邀请同事加入**：下一步邀请同事加入，共同制作解决方案。
 # 协作需求
-- **邀请同事加入**：主持人提出下一步开始邀请同事加入，需成员配合确认参与意愿，会后由主持人逐一沟通了解意向。
-- **线下继续学习**：主持人提议会议时间已长（约一小时），计划转为线下继续共同学习，需成员配合安排线下时间与地点。
-- **修订文件确认**：主持人要求成员自行查看已修订的303相关文件，并在对应条目上打勾确认，需成员配合完成审阅反馈。
-- **任务安排调整**：主持人指出任务优先级需调整（如洛阳行程应排到第二项），需相关成员配合修改任务安排。
-- **活动费用统计**：主持人提出需统计活动页面费用（涉及两个未发送账单），需成员配合提供费用数据以完成统计。
+- **邀请同事加入**：主持人提出下一步邀请同事加入，共同制作解决方案，需成员会后确认有谁愿意参与，并安排下道工序后即可加入。
+- **学习介绍修改配合**：主持人已修改学习介绍并将「我们是谁」提到最上面，需相关成员根据修改后的参数同步调整公众号、抖音任务及可视化学习方案和工具。
+- **任务分配调整**：主持人指出部分任务地方性不大，需张经理（张张经理）修改任务安排，将下周洛阳行程相关事项排到第二项。
+- **课程开发与执法队伍组建**：组建执法队伍为下月主要任务，需招聘20多位师傅，需成员配合确定路线、修订纲领章程，并安排任务运行。
+- **待遇与休假确认**：待遇为上班5000元、额外奖励及提成，休假为周五半天加周末两天，需成员确认是否接受该安排。
+- **会议纲要修改**：主持人询问会议纲要是否还需修改，需成员反馈意见后确定是否调整。
 # 待确认与风险
-- **工作方向确认**：主持人提出当前工作方向可能偏了，需要确认是否调整，尚未形成结论。
-- **任务工作量评估**：需考虑现有任务的工作量是否可承受，具体评估标准未定。
-- **活动费用统计**：活动费用尚未统计，需统计剩余费用（原文提及"两个零一乘二"需计算）。
-- **会议纲要修改**：会议纲要是否需要修改仍在讨论中，未拍板。
-- **任务分配安排**：任务分配的具体安排待确认，部分任务（如课程开发）的负责人与分工未明确。
-- **账单发放阻塞**：两个账单未发送（全场活动优美和棒棒糖待遇），发放完成才能入职，薪资待遇留待月会再发。</t>
+- **工作方向是否偏了**：主持人提出当前工作方向可能偏了，需要考虑工作量，但未明确具体偏差点与调整方案，待后续确认。
+- **会议纲要是否还需修改**：会上有人提出「这个会议纲要还要改吗」，未形成结论，修改与否待定。
+- **是否要报上上**：主持人提出「要不要报上上」，大家未好好讨论，是否申报未决。
+- **社区环境与成员准入**：强调「人不出去怎么学习」，需防止坏人进入，但准入机制与执行方式未议定。
+- **任务分配与条件差异**：提到任务分配时「可能他们菜品条件不太一样」，各任务条件差异对分配的影响未明确。</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>29.6</v>
+        <v>31.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4999/1743</t>
+          <t>4999/1909</t>
         </is>
       </c>
     </row>
@@ -8646,44 +8607,44 @@
       <c r="C24" t="inlineStr">
         <is>
           <t># 就诊概况
-48岁男性患者张春和，在成都轻工研究所从事科研工作，因上腹反复不适4年、近3个月持续加重，于今日在消化内科初诊。患者主诉心窝处烧灼样疼痛，进食冷、硬、刺激性食物或工作紧张劳累时诱发，白天发作、无夜间痛醒，疼痛可忍受，有完全不痛的时候；近4年出现两次黑便（一年前、三个月前各一次），每次持续约一个月，均住院治疗后转黄；最近两个月出现呕吐，吐出酸水样物及所食食物，夜间呕吐后舒适，偶有隔夜食物吐出。近期服用斯达舒（剂量从每日两次每次一颗增至每日四五次）效果不佳，另服用过奥美拉唑（武汉药厂产）、阿莫西林及医务室自配胃炎合剂，停药后症状反复。初步考虑上消化道疾病可能，需进一步检查明确，已预约后天胃镜并留大便检查排查出血。
+48岁男性患者张春和，职业为成都轻工研究所科研人员，因上腹反复不适4年、近3个月加重，于消化内科门诊初诊。患者自述心窝处烧灼样疼痛，进食冷、硬、辛辣食物或工作紧张劳累时诱发，近3个月白天发作、无夜间痛醒；曾两次黑便（一年前、三个月前各一次），近两月呕吐酸水样物，含当日或隔夜食物。近期服用斯达舒、奥美拉唑、阿莫西林及胃炎合剂，效果不佳。初步考虑上消化道疾病可能，需进一步检查明确，本次就诊拟行大便潜血检查及胃镜检查。
 # 病史与背景
-- **现病史**：上腹反复不适4年，每年春季多发，近3个月持续；疼痛位于心窝处，有烧灼感，进食冷、硬、刺激性食物或工作紧张劳累时诱发，白天发作、无夜间痛醒，疼痛可忍受，有完全不痛的时候。
-- **黑便史**：近4年出现两次黑便，一次在一年前，一次在三个月前，每次持续约一个月，每日最多两次，大便干、形状正常；两次均住院治疗，住院后大便转黄，第一次住院约10天，第二次住院两三天。
-- **呕吐史**：最近两个月出现呕吐，吐出酸水样物，含早晨或中午所食食物，晚上呕吐后舒适，偶有隔夜食物吐出。
-- **既往史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；小学时因扁桃体炎在儿童医院服用磺胺药后左手起红疹，持续半个月，医生诊断为药物过敏，此后禁用磺胺药。
-- **个人史**：双眼近视400度，平时不怎么戴眼镜；偶尔口腔溃疡，贴小紫烟（西瓜霜）就好；吸烟史，以前每天一包，现限制在10支以内，考虑逐步戒烟；偶尔饮酒，平时不喝；喝淡茶，每天泡两次；26岁结婚，有一子，爱人及孩子身体健康。
-- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；一位婶婶（叔叔的爱人）患胃癌，患者担心自己是否也患胃癌。
+- **现病史**：上腹烧灼样疼痛4年，每年春季多发，近3个月持续；疼痛位于心窝处，进食冷、硬、辛辣食物或工作紧张劳累时诱发，白天发作、无夜间痛醒，疼痛可忍受，工作轻松时有完全不痛的时候。
+- **黑便史**：两次黑便，一次在一年前、一次在三个月前，每次持续约一个月，每日最多两次，大便干、形状正常；两次均住院两三天后大便转黄。
+- **呕吐史**：近两个月出现呕吐，吐出酸水样物，含早晨或中午所食食物，晚上吐出后舒适，偶有隔夜食物吐出。
+- **既往史**：16岁患甲肝，在三医院住院一个月治愈，出院时各项指标正常，此后体检肝功均正常；无手术史。
+- **过敏史**：小时候因扁桃体炎在儿童医院服用磺胺药后左手起红疹，持续半个月，医生诊断为药物过敏，此后不能服用磺胺药。
+- **个人史**：出生于成都，一直在成都生活，在成都轻工研究所从事科研工作，工作紧张、常加班熬夜；吸烟由一天一包减至10支以内，计划逐步戒烟；平时不饮酒，应酬时少量；每天泡两次淡茶；26岁结婚，爱人及孩子身体健康，三口人住两房一厅。
+- **家族史**：父亲76岁有低血压，母亲75岁有冠心病（服药控制良好），弟弟身体健康；婶婶（叔叔的爱人）有胃癌，患者担心与此有关。
 # 诊断与检查结果
-尚未确诊，考虑上消化道疾病可能，需进一步检查明确。严医生建议留大便检查以排查出血，因患者曾出现两次黑便；并预约后天做胃镜，因患者爱人可请假陪同，胃镜后安排张医生查房。患者担心自己是否患胃癌（因婶婶有胃癌病史），严医生解释婶婶是叔叔的爱人，与患者无血缘关系，不必担心；患者还担心是否需要手术，严医生表示需等检查资料全面后再判断，若能药物控制则可不手术。
+初步考虑上消化道疾病可能，需进一步检查明确。患者有两次黑便史，需排查消化道出血；有胃癌家族史（婶婶，无血缘关系），患者本人担忧，严医生解释婶婶无血缘关系，不必担心遗传问题。患者担心是否需要手术，严医生表示待检查资料全面后再判断，若能药物控制则不需手术。
 # 治疗方案与医嘱
-- **检查安排**：留大便检查以排查出血；预约后天做胃镜，因患者爱人可请假陪同，胃镜后安排张医生查房。
-- **生活方式与饮食**：建议戒烟，因吸烟对身体不好，对疾病有好处；建议尽量少喝酒，因酒对胃肠道疾病影响较大；注意休息，避免熬夜，因熬夜对疾病有影响。
-- **复诊安排**：严医生将总结病情向张医生（指导教授）汇报后再商定治疗意见。
+- **检查安排**：留大便做潜血检查，以排查出血；胃镜预约在后天进行（因患者要求爱人陪同）。
+- **生活方式与饮食**：建议减少吸烟、饮酒，避免工作过度劳累，以配合治疗。
+- **复诊安排**：严医生将总结病情后向上一级张医生（指导教授）汇报，再商定下一步处理意见。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 斯达舒 | 每次一颗（后增至每日四五次） | 每日两次（后增至每日四五次） | 口服 | 初服有效，后效果不佳，剂量越加越多仍效果不好 |
-| 奥美拉唑 | — | — | 口服 | 武汉药厂产（国产），停药后症状反复 |
-| 阿莫西林 | — | — | 口服 | 停药后症状反复 |
-| 胃炎合剂 | — | — | 口服 | 医务室自配，停药后症状反复 |
+| 斯达舒 | — | 每日四五次（原每日两次每次一颗，后加量） | 口服 | 初服有效，后效果不佳，加量后仍效果不好 |
+| 奥美拉唑 | — | — | 口服 | 武汉药厂产，国产 |
+| 阿莫西林 | — | — | 口服 | — |
+| 胃炎合剂 | — | — | 口服 | 医务室自配 |
 # 复诊与预警信号
 ## 复诊与随访安排
-- **胃镜**：预约后天做，因患者爱人可请假陪同，胃镜后安排张医生查房。
-- **大便检查**：留大便检查以排查出血。
-- **病情汇报**：严医生将总结病情向张医生汇报后再商定治疗意见。
+- **胃镜检查**：后天进行，需爱人陪同。
+- **大便潜血检查**：留大便做潜血检查。
+- **病情汇报**：严医生将总结病情后向上一级张医生汇报，再商定下一步处理意见。
 ## 预警信号
-- ⚠️ 黑便：患者曾出现两次黑便，需排查出血。
-- ⚠️ 呕吐：最近两个月出现呕吐，吐出酸水样物及所食食物。
+- ⚠️ 再次出现黑便需及时就医。
 ## 需要观察的变化
-- 观察大便颜色变化，如有黑便需及时就医。</t>
+- 观察腹痛、呕吐症状变化，如有加重或新发出血迹象及时联系。</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>48.4</v>
+        <v>55.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10297/1682</t>
+          <t>10297/1425</t>
         </is>
       </c>
     </row>
@@ -9022,76 +8983,109 @@
       <c r="C25" t="inlineStr">
         <is>
           <t># 讲座概况
-肖楠（基金经理）面向机构投资者作投资理念与框架汇报，主题为过去一年的研究布局、投资框架的反思与更新，并解答投资者疑问。讲座围绕四大研究布局（互联网、财富管理行业、新消费、高端制造）展开，核心主张包括：反对“抱团”与“均值回归”两种市场观点，认为收益率呈幂律分布而非正态分布；投资框架需不断扬弃，应纳入隐性长期变量并承认无法定价的X factor。关键锚点：美国股市200年价值增量由4%的公司贡献；海螺水泥波段操作案例；顺丰、美的在疫情中的曲率拐点。对听众的意义在于帮助投资者理解基金经理的认知升级与选股逻辑，而非追逐短期研判。
+肖楠在面向机构投资者的专项讨论会上作投资理念与框架汇报，主题为过去一年的研究布局、研究成果及投资框架的反思与更新。他开宗明义指出，投资者普遍关心的“What happen next”式问题答案用处有限，因为知识与信息之间存在巨大鸿沟；真正值得研究的是标的基本面是否变化、投资逻辑有无更新、自身框架是否需修正等可研究问题。他介绍市场上基金经理理念大致处于巴菲特务实派与索罗斯务虚派两个极端之间，自认偏巴菲特一侧，并明确反对“抱团”与“均值回归”两种流行观点，认为其定义不本质，收益率呈幂律分布而非正态分布——美国股市200年价值增量由4%的公司贡献。汇报围绕互联网、财富管理、新消费、高端制造四大研究布局展开，并分享五点投资框架反思：商业模式分类不完备、商增视角更本质、终局判断与中期机会的平衡、长期变量（如国运）的忽视、深度价值可能长期无效及企业X factor的存在。对投资者而言，本次汇报旨在让其了解基金经理的研究积累、看问题角度及理念框架的持续升级，以检验言行是否一致。
 # 核心观点与论证
 ## 知识与信息的鸿沟
-- 肖楠认为投资者关心的“What happen next”问题用处不大，因为听到的答案只是信息而非知识，知识与信息之间存在巨大鸿沟。
-- 他举例：自己看好某板块是基于知识，但投资者得到的只是“肖楠看好某某”的信息，且观点会随知识更新而改变，投资者可能一年后才知晓。
-- 他将问题分为重要不重要、可研究以及难以研究四类，自己关心标的基本面变化、投资逻辑更新、投资框架修正等可研究问题。
-## 基金经理的两大流派
-- 肖楠将基金经理分为以巴菲特为代表的极端务实派和以索罗斯为代表的极端务虚派，自己处于中间偏左位置。
-- 务实派认为股票是企业所有权的一部分，价值来源是企业未来现金流，短期波动随机不值得研究，应买入长期持有。
-- 务虚派认为股票是筹码，价值来源于其他交易者的看法，交易代表信息，应研究交易者基于基本面的行为。
-- 肖楠强调务实与务虚没有高下之分，做好的都是大师，做不好都是东施效颦。
-## 反对“抱团”
-- 肖楠认为“抱团”定义不本质，基金经理之间是竞争关系，主观上不可能抱团，如打电话给嘉实王经理商量一起买股票不现实。
-- 同一基金公司买同一板块不叫抱团，研究员推荐股票获广泛认可后大家买入是正常现象，否则需抽取幸运基金经理才能买。
-- 抱团只是截面数据，忽略时间维度，如自己8年前、5年前已买入，后来者蜂拥而至并非抱团。
-## 反对“均值回归”
-- 肖楠认为均值回归是“特别不本质的局部正确”，短期看涨多了要跌，但无法解释长线牛股10年涨10倍、20倍、50倍、100倍的现象。
-- 举例：某商学院老师在海螺水泥上做波段，过去十年赚两三倍，但2016或2017年卖出后，两年内股价涨了五六倍，再也没买回来。
-- 肖楠指出收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献，若挖掉这4%的公司，美国股市200年没有涨。
+- **知识 vs 信息**：肖楠认为，投资者关心的"What happen next"类问题，得到的答案对他用处不大——对肖楠而言看好某板块是基于相关知识（`knowledge`），但对投资者而言得到的只是一条"肖楠看好某某"的信息，知识与信息之间存在巨大鸿沟。
+- **观点会随知识更新而变**：肖楠举例，今天看好某板块，明天可能因新知识增加而修正判断；但投资者可能等一年甚至更久才知道观点已变，因此这类答案对投资者实际价值有限。
+## 研究问题的分类框架
+- **四类问题划分**：肖楠基于自己的研究框架，将问题分为重要/不重要、可研究/难以研究四个象限，只研究"重要且可研究"的问题。
+- **真正关心的问题**：标的基本面是否发生变化、投资逻辑有无更新、对标的的认知是否更深入领先；作为基金经理，最关心自己的投资框架有无值得修正之处。
+- **框架仅针对个人**：该分类只针对肖楠个人——例如基于宏观变量做资产配置的人，会认为美联储利率变化对市场的影响是既重要又可研究的问题。
+## 两大投资流派
+- **两个极端**：市场上基金经理的理念方法大致处于两个极端之间——以巴菲特为代表的"极端务实派"和以索罗斯为代表的"极端务虚派"。
+- **巴菲特一派**：股票是企业所有权的一部分，价值来源是企业价值即未来现金流；短期波动是随机的、不值得研究，研究重点应放在公司生意、管理层上，买入长期持有直到投资逻辑变化。
+- **索罗斯一派**：股票是筹码，价值来源于其他交易者对筹码的看法；交易代表信息，股价波动代表信息，不仅要研究基本面，更要研究交易者基于基本面的行为，通过交易与市场对话、试错、获利。
+- **肖楠的定位**：大部分基金经理包括肖楠都处于两个极端中间某位置，肖楠自认偏巴菲特一侧；务实还是务虚没有高下之分，"做好的都是大师，做不好都是东施效颦"。
+## 反对"抱团"观点
+- **定义不本质**：肖楠认为"抱团"这个定义不本质——如果对现象下定义不本质，会导致研究误入歧途，如同把"一叫太阳就出来"的动物命名为"光明使者"，会让人误以为宰了它太阳就不出来。
+- **主观上无抱团意愿**：基金经理之间是竞争关系，每个基金经理都想买跟别人不一样的东西并获得市场认可；"打电话给嘉实基金的王经理说我们抱在一起买股票"在主观上不可能。
+- **同一公司买同板块不算抱团**：研究员推荐股票、多位基金经理认可后买入是公募基金正常运作方式；若定义为抱团，则"研究员每推荐一个股票就抽取三位幸运基金经理去买"的荒谬做法就变得必要。
+- **截面数据忽略时间维度**：肖楠举例，自己8年前、5年前就买入某类标的，突然一天大量资金蜂拥而至"跟我们紧紧抱在一起"，其实自己也一脸懵；拉长时间看，A股和海外股市都有"五朵金花""眉飞色舞""长牛的医药消费"等现象，非常稀松平常。
+## 反对"均值回归"观点
+- **均值回归是局部正确**：短期看K线图确实涨多了要跌、跌多了要涨，但拉长看无法解释10年涨10倍、20倍、50倍、100倍的长线牛股。
+- **海螺水泥案例**：肖楠的研究员是某商学院毕业生，其课程老师过去10年在海螺水泥上做波段赚了两三倍，技术指标自己编的非常准；2016或2017年涨一波后老师卖掉等回调，结果两年时间股票涨了五六倍，老师再也没能买回来——"均值回归90%的时间都正确，那10%的错误依然让你代价惨重"。
+- **收益率是幂律分布**：投资核心是找到摆脱"涨多了又跌、跌多了又涨"局部规律的特别长线超级大牛股；美国股市200年价值增量由4%的公司贡献，把4%的公司挖掉，200年来美国股市没有涨。
 ## 四大研究布局
-- **互联网**：全球只有中国和美国能做成巨大产业，中国已迭代三代企业（流量、运营、算法），如门户网站、阿里淘宝、字节拼多多，港股通开通后可投资更多公司。
-- **财富管理**：中国进入小康，人均收入中位数提升5%-10%将带来巨额剩余财富，行业空间远超想象。
-- **新消费**：新一代消费公司从CEO到组织架构、经营理念与匮乏年代企业完全不同，未来会越来越多。
-- **高端制造**：中国是全球几乎唯一拥有全产业链的国家，很多领域已占据主导地位，未来空间可见。
-## 投资框架的反思
-- **商业模式分类不完备**：肖楠将生意分为坐地收钱、苦尽甘来、燃烧自己照亮别人三类，但承认没有一劳永逸的坐地收钱生意，爱马仕也受设计师影响，长期看所有企业都会死去。
-- **商增视角更本质**：从商增角度理解商业模式更本质，企业成长中商增过快会导致失败，柯斯定理说明商增到一定程度企业无存在必要。
-- **长期变量被忽略**：长期变量（如国运、文化背景）可能解释相当部分收益率来源，需保持谦卑并研究隐性长期变量，如日本、德国没有巴菲特、索罗斯。
-- **深度价值可能无效**：深度价值只是结果，原因不变则结果最好是不输，去年投的深度价值标的表现很差，打了问号。
-- **小企业X factor**：驱动企业增长且不被线性描述的因子，经典模型无法定价但必须承认其存在，否则会陷入估值与基本面的两难。
+- **互联网**：全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业——第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）；开通港股通后，以前A股无法投的公司现在可以投，不能容忍在这个领域错失机会。
+- **财富管理**：中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，由于巨大基数效应和收入分布密度效应，会有巨额剩余财富有待专业机构管理，行业潜在空间远超想象。
+- **新消费**：从匮乏年代走出来的第一代、第二代消费品公司与富裕年代诞生的新消费公司完全不同——从CEO的想法理念、组织架构、基层执行人员到生产方式、营销方式都截然不同；不是产品够新才叫新消费，而是这类公司从CEO到组织架构、经营理念完全不一样。
+- **高端制造**：中国是全球几乎唯一拥有全产业链的国家；深入到制造业细分领域看，中国在很多领域已不是被卡脖子，而是"客气一点讲叫占据主导地位"；与10年前"10亿双袜子换台飞机"的理解完全不同，欧美日企业手中的市场份额"已经是中国企业碗里的肉了"。
+## 新消费领域的研究发现
+- **产品差异被低估**：外人看两家公司产品差不多（都卖笔、都卖电饭锅），但收入利润体量差距巨大；深入研究发现，在产品经理团队或CEO眼中，自家产品与竞争对手产品存在巨大鸿沟，这些差异在三年、五年、十年维度会被放大得非常非常大。
+- **行业格局差异**：传统消费领域龙头赚钱、龙二龙三也赚钱是稀松平常的现象；新消费领域同样巨大的行业可能只有两家公司，一家赚很多钱，另一家完全不挣钱、不知道该怎么挣钱。
+## 商增视角理解商业模式
+- **商增过快导致失败**：企业总是要成长，但成长过程中有些企业商增速度远超另一些企业，商增过快会导致企业走向失败；研究大量企业失败案例后发现，商增是理解商业模式非常重要的角度。
+- **商增更本质**：有些企业从诞生到收入和利润涨100倍，结构跟诞生时没有特别大区别，商没有怎么增加就能放大100倍；另一些企业扩张过程中商增剧烈，增到一定程度后"科斯定理就告诉我们这个企业已经没有存在的必要了"。
+## 对商业模式分类的反思
+- **三类生意划分**：肖楠过去把生意分为三类——坐地收钱（最喜欢买）、苦尽甘来、燃烧自己照亮别人（不值得买）；至今依然这样划分，也相信对商业模式的理解非常好。
+- **框架的不完备性**：世界上没有一劳永逸的坐地收钱生意，极端稀缺或稀少；哪怕爱马仕这样的企业，一个设计师的好坏也可能给未来五年十年销售带来非常大影响；长期看所有企业都要死去，单一从"买千秋万代企业"维度出发会错失很多机会。
+## 对终局判断的反思
+- **错过中期10倍机会**：因强调企业终局可能不太好或看不清楚，放弃了一些中期投资机会，甚至中期机会是10倍涨幅也没把握住；复盘发现完全可以在终局判断前提下做出漂亮投资。
+- **具体案例**：某企业产品跨代领先竞争对手，肖楠当时判断这种领先不能长期保持、竞争对手会赶上来、行业格局会变差、ROE会剧烈下降——这一判断完全正确，一两年内确实如预判发生；但从下终局判断到后来，该企业足足涨了十几倍，中间过程完全错过。
+- **调整方向**：在坚持对终局重要性判断的基础上，争取研究格局演进的阶段性特征来把握投资机会；可通过紧密跟踪认知快速迭代、识别里程碑式事件来提高胜率，在比较中期的时间内获得好的投资回报率。
+## 长期变量的重要性
+- **为什么美国出投资大师**：日本、德国、越南没有出巴菲特、索罗斯这样的投资大师，美国有；中国股市短短20多年也诞生了一批长线收益非常好的基金经理，但放到台湾、日本、韩国不一定有同样收益率——可能有特别长线的变量解释了相当一部分收益率来源。
+- **国运是隐藏变量**：西方世界过去对中国的判断中，没有人预料到中国和平稳定高速发展30多年、40年；中国每一年都遇到困难，但最后都发现高速发展是事实，这个隐藏的巨大变量称作"国运"有点不对但也有一点对。
+- **茅台案例**：把过去买茅台赚钱的人写的回忆录中的投资逻辑全部列出——A说因为便宜、B说因为产品好、C说因为商业模式好——这些逻辑加在一起解释不了过去十年、二十年茅台如此巨大的涨幅；别的一些股票也有类似逻辑，为什么涨得没有茅台多？可能有一个更大的变量（宏观经济背景、文化背景、品牌背景）在后面起作用。
+- **奢侈品牌案例**：LV、爱马仕讲的故事是"祖上给皇上当过马夫、给娘娘当过皮匠"，但给的是英国、法国这些老牌资本主义国家的皇上——因为他们的军舰当年横扫全世界，所以他们的皇上是最厉害的皇上，皇上的皮匠是最厉害的皮匠。
+- **白酒出海逻辑**：30年前洋酒刚进入中国时，中国土豪兑雪碧喝，因为难喝才兑雪碧，但难喝还要喝是因为人家的文化是强势文化；如果有一天中国国力强盛到能在人家十二海里外做军事演习，就可以讲"纯粮固态发酵的酒才是好酒，whisky、白兰地、清酒都是液态发酵法做出来的，特别不值钱"这个故事。
+- **研究调整**：未来做研究时，会把一些特别隐性的、在十年维度上起作用的长期变量纳入研究框架；"要经常对市场保持谦卑"，但也保持大胆想象——20年前不敢想中国GDP超过日本，现在可以想中国好的消费品出海。
+## 深度价值可能长期无效
+- **深度价值只是结果**：深度价值只是一个结果，如果导致深度价值的原因不变，那么深度价值最好的结果也就是不输了；过去看深度价值投资方式不是特别成功，是因为导致深度价值的原因不变。
+- **投资结果很差**：过去投了一些认为是深度价值的标的，包括去年也投了一些，结果非常差，产生了很大启发和刺激；"深度价值某种成长可能会不会无效"打了问号，没有得出结论。
+## 企业增长的X factor
+- **经典模型是线性假设**：做DCF、DDM都是线性假设，无非增长率是12%、13%、14%还是15%、16%、17%的区别；但拉长到10年视角，企业发展是一条非常漂亮的曲线，而所有经典投资模型都没有一个变量隐含对企业发展曲率的估计。
+- **X factor的定义**：驱动企业增长且不被线性描述的因子，经典投资理论模型无法给这些因素定价，但在长期起作用的就是这些；即使无法有效定价，也一定要承认它的存在，否则会陷入"企业挺好但估值贵、企业便宜但基本面烂"的挣扎。
+- **顺丰案例**：疫情时只有顺丰能送，一下子把业绩和估值甩出一大截；如果做线性外推，无非是今年增速快一点（15%对13%），但拉长看就是在关键点上突然甩出来。
+- **美的案例**：过去格力一直是老大，美的做渠道扁平化、T+3一直没看到成果；突然疫情来了，美的占有率一下上去、超过格力——当企业在埋头做事还没体现到报表时，往往忽略这些事情未来可能产生的重大影响。
+- **第二第三增长曲线**：5年前、10年前大家说某企业产品渗透率已很高、利润率已很高，但到今天看当年说的那些全部没实现，企业长出了第二生长曲线、第三生长曲线，还在找新的——这就是有X factor的企业；经常强调的超额认知就来自这些方面。
 # 金句总结
 &gt; “知识和信息之间是有着巨大的鸿沟的。”
-- 背景：开场阐述投资者关心的“What happen next”问题用处不大时。
+- 背景：开场阐述投资者关心的“What happen next”类问题答案用处不大，因为投资者得到的只是信息而非知识。
 &gt; “务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。”
-- 背景：介绍巴菲特与索罗斯两大流派后强调理念无好坏。
+- 背景：对比巴菲特务实派与索罗斯务虚派两大投资流派后，强调理念本身无好坏之分。
+&gt; “如果一件事情我们就对现象去下一个定义，如果这个定义不本质，会导致我们对这个东西的研究误入歧途。”
+- 背景：反对“抱团”这一市场流行说法，认为该定义不本质、不说明问题。
 &gt; “均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。”
-- 背景：反对均值回归，以海螺水泥波段操作案例说明。
-&gt; “收益率是幂律分布的，不是正态分布的。”
-- 背景：解释为何反对均值回归，强调长线牛股贡献绝大部分收益率。
-&gt; “我们一定要把底线的风险搞好。我们一致同意的就是这个东西它不可被定价，它不能被定价。”
-- 背景：回答企业家精神观察心得，强调谨慎归因、不轻易定价。
+- 背景：反对“均值回归”观点，以研究员老师在海螺水泥上做波段、最终两年错过五六倍涨幅为例。
+&gt; “200年以来，美国股市的价值增量，是由4%的公司贡献的。”
+- 背景：论证收益率呈幂律分布而非正态分布，投资核心是寻找长线超级大牛股。
+&gt; “这个世界上其实没有一劳永逸的坐地收钱的生意。”
+- 背景：反思“坐地收钱、苦尽甘来、燃烧自己照亮别人”三种商业模式分类的不完备性。
+&gt; “我们尽管穷尽了我们所有的智慧、所有的精力去力求探究我们的收益率的来源，往往依然是忽略了一个巨大的变量在后面起作用。”
+- 背景：反思长期变量（如国运、文化背景）对收益率来源的贡献，主张对市场保持谦卑。
+&gt; “驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。”
+- 背景：提出企业增长存在“曲率”与X factor，经典投资模型无法纳入这些因素但它们在长期至关重要。
 # Q&amp;A 环节
-**听众**：您刚刚有讲到是在对于终局结果的重视的过程中，也更加去关注格局演进的过程中阶段性的特征，中期投资机会，请问您能对这一点再详细描述一下吗？
-**肖楠**：这个想法最早来自我们过去错过了一些特别大的机会，我们判断这些行业的终局可能不大行，但明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，这类企业有一些重要特征被我们忽略：比如某一代产品当时领先，后来确如我们所料被人追上，但企业深深做出了第二增长曲线，且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。所以我们后来渐渐开始承认终局可能没有那么强，但在这种前提下依然能做出好的投资，希望未来不要再错过类似机会。具体标的不太好说，确实有一两个标的给我们带来极大刺激。
-**听众**：您在年报中也讲到过，坚定持有优秀乃至伟大的公司。请问您是否能对于这个优秀乃至伟大的公司的判断标准，有一些具体的财务指标？
-**肖楠**：伟大公司是在财务指标里面看不出来的。我举一个例子，不能说具体企业：A企业和B企业同属一个大行业但不同细分子行业，投资逻辑很像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高。但A公司每年有高额研发支出，关键技术指标以非常强的速度迭代，研发项目很多是前沿方向，技术掌握在德国人、日本人手里；B公司不怎么研发，靠管理精益求精，业内络绎不绝来学习但学不会。这两家都是国企，A公司在发展初期被德国人、日本人狠狠坑过，从董事长到技术骨干都有强烈的产业报国、技术报国理想，从跟着学、越做越强到超越对手、对手来学、做全产业链布局，这种企业堪称伟大。
-**听众**：我们是全市场基金，能否介绍一下这个产品的投资逻辑呢？对于消费以外的行业的选股，主要是基于什么逻辑呢？
-**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的“不可能三角”、企业三阶段、三种商业模式。只不过消费行业只许买消费，所以只能在消费行业里选，两者的选股逻辑完全一样，没有什么区别。
-**听众**：您是怎么看待血制品行业的竞争壁垒呢？
-**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开，因为我们研究不是特别多，相比之下我们买了另外一些强壁垒的公司。
-**听众**：在管理行业能否再具体讲一下呢？
-**肖楠**：我们只就血制品这个行业，研究不是特别多，因为我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有一些特别冲突的观点。
-**听众**：农林牧渔行业是有所提升，请问您对这个行业的观点能够给我们讲一下吗？
-**肖楠**：这行业太大了，农林牧渔行业的提升是因为牧原股份，就那一只股票。不是我先看好农林牧渔行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。
-**听众**：您能够再具体讲一下生意模式里边商增和商减的这个分析吗？
-**肖楠**：用直白的理论讲，你们都是企业里的打工人，能深切感受到：企业从小到大，部门越来越多，以前三五个部门现在十几个，中层干部一大堆，传达效率变低，内部腐败开始出现。企业为解决腐败要设巡视检查部门，又多一个部门，部门里的人要加工资提级别。企业扩张往下游或上游做，要多一个副总裁，又多很多部门。有些生意收入10亿和100亿时没多几个部门，有些企业不需要设那么多高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的，比如互联网大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生。做得不好的那家从一开始就没考虑好企业大了以后商增怎么处理。我特别建议大家去读一读党史，看看这个组织怎么从国民革命时期、抗战时期一直走到现在还能保持活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年这种事在很多国家都会发生。
-**听众**：您讲到伟大的企业的增长曲线，您能否对于这个曲线的情况再具体跟大家讲一下呢？
-**肖楠**：有些企业过去几年每年增长20、15、17.5，都是线性的，但站10年周期看，跟竞争对手拉开极大差距。举例：疫情时只有顺丰能送，一下子把业绩和估值甩出一大截；家电领域格力一直是老大，美的做渠道扁平化、T+3一直没看到成果，疫情一来美的占有率哗一下就上去了，超过格力。这些企业在埋头做事还没体现到报表时，我们往往忽略未来可能产生的重大影响。曲率拐就拐在那一下子，这些伟大的企业都是在特别特殊的时候拐上去的，就像平时走路突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡。
-**听众**：您刚刚讲到财富管理行业，能否对这个行业具体展开，讲一下投资逻辑和投资机会呢？
-**肖楠**：财富管理行业这个话题特别大，而且行业是分层的，顶级富豪、普通中产阶级、中低收入人员的财富管理怎么做，都有不同的公司和商业模式。我们最早研究保险时发现，有些保险公司一个业务员一单能签七八千首期保费，有些只有两三千，差距巨大。调研后发现，同样是卖保险，背后的结构设置、激励机制、文化差异超级大。去年发基金时，有些渠道经理过来调研问的问题超级专业，有些永远问下半年是涨是跌、明年是牛市还是熊市。财富管理行业最大的逻辑在于财富分布超级不均匀，头部公司可能一口气拿掉行业增量的绝大部分，第二名只能拿到剩下的20%的80%。在这种特别偏激的行业里，有可能诞生特别大的企业。但很遗憾，我们有些产品因为监管和法律规则的原因不能投类似标的，未来合同设置更清晰时可能会有所体现。
-**听众**：您刚刚讲到曲线的方面，第二第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问肖楠总在观察这个指标的方面会有什么心得和把握呢？
-**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因，不要因为一个企业经营成功就说企业家特别厉害，就像不要因为基金经理业绩好就说他特别厉害。一定要把所有能归因到数据里的客观指标的因素都归因完，再谨慎评价比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为企业家在所以公司就能值多少。我始终强调的是避免错误归因，避免因为对企业家认可而犯投资错误，一定要把底线风险搞好。这些虚的因素（技术进步、企业家精神）在什么时候考虑？在所有客观归因都尽量穷尽以后再说。我们只能在有限范围内做两两比较，比如两家公司做同样生意、同样产品，可以比较两个企业家的水平高低、理念先后，找认可的那一家，不要跨行业、跨业务、跨产品比较。不要什么事情都归结到企业家身上，要谨慎使用“企业家精神”“伟大企业”这些词，在特别极端的时候它可能是信仰上的支持，但尽量不要去用。</t>
+**听众**：您刚刚讲到在重视终局结果的同时，也更加关注格局演进过程中的阶段性特征和中期投资机会，能否再详细描述一下？
+**肖楠**：这个想法最早来自我们过去错过的一些特别大的机会。我们当时判断某些行业的终局可能不大行，结果判断对了，但在两三年的时间里深深错过了十几倍的涨幅，这非常要命。复盘时发现，当时完全可以在考虑终局可能没那么好的前提下，依然做出漂亮投资。这类企业有一个重要特征是我们当时忽略的：某一代产品领先后来确实被追上，但企业做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。这让我们很惊讶，也刺激很大。所以后来我们渐渐开始承认终局可能没那么强、不会像一劳永逸躺着收钱那么强，但依然能做出好的投资，希望未来不要再错过类似机会。具体标的不太好说，确实有一两个标的给我们带来极大刺激。
+**听众**：您在年报中也讲到坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有一些具体的财务指标？
+**肖楠**：伟大公司在财务指标里是看不出来的。我举一个例子，不能说具体企业：有两家公司同属一个大行业但不同细分子行业，投资逻辑很像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高，精细化管理能力都非常好。但有一点不同——B公司不怎么研发，靠管理上精益求精做到成本低，壁垒在于业内络绎不绝来学习但学不会；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人、日本人手里。有意思的是这两家都是国企，A公司在发展初期被德国人、日本人狠狠坑过，从董事长到技术骨干积攒了强烈的产业报国、技术报国情绪，从跟着学、越做越强、超越对手，到对手跑来学、做全产业链布局，写下来就是产业史诗。这种企业堪称伟大。我们过去能看到非常多这样的企业，中国人在一点点往前拱，这些人不是想今年赚三五个亿，而是一门心思往前做。
+**听众**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对消费以外行业的选股主要基于什么逻辑？
+**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的不可能三角、企业三阶段、三种商业模式这些。只不过消费行业基金只许买消费，所以只能在消费行业里选。两者的选股逻辑完全一样，没有什么区别。
+**听众**：您怎么看待血制品行业的竞争壁垒？
+**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开了，因为我们的研究不是特别多。我们也找了一堆强壁垒的公司，相比之下买了另外一些。
+**听众**：在管理行业能否再具体讲一下？
+**肖楠**：血制品这个行业我们研究得不是特别多，因为我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有一些特别冲突的观点。
+**听众**：农林牧渔行业持仓有所提升，请问您对这个行业的观点？
+**肖楠**：这行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。我不能在公开场合讲具体股票的投资逻辑。农林牧渔行业的提升不是因为我先看好这个行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。
+**听众**：您能再具体讲一下生意模式里商增和商减的分析吗？
+**肖楠**：用直白的话讲，你们都是企业里的打工人，能深切感受到：企业从小到大，部门越来越多，以前三五个部门现在十几个，中层干部一大堆，上面分领导、副总裁，下面一大堆基层部门，传达效率变低，内部腐败开始出现。企业为了解决这些问题要设巡视检查部门，又多一个部门，部门里的人干三五年要加工资提级别，这么多部门老总今年提哪个明年提哪个。企业发展到一定程度要往下游或上游扩张，多一项业务就要多一个副总裁，又多很多部门。有些生意收入10亿和100亿时没多几个部门，有些企业不需要设那么多高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如有些行业剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生。做得不好的那家从一开始就没考虑好企业大了以后商增怎么处理，导致山头林立；另一家基本是高度中央集权，CEO有非常强大的情报部门，知道每件重要事情细入基层是怎么回事。我特别建议大家去读党史，看看这个组织怎么从国民革命时期、抗战时期一直走到现在还能保持活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年这种事在很多国家都会发生。
+**听众**：您讲到伟大企业的增长曲线，能否再具体讲一下？
+**肖楠**：有些企业每年看都是线性增长，今年增长20、明年15、后年17.5，差的时候增长3、5。但站到10年周期看，这个企业跟竞争对手之间拉开了极大差距。举个例子，快递行业，疫情的时候只有顺丰能送，没疫情时看不出来，一下子顺丰的估值和业绩把竞争对手甩出一大截。家电领域也是，格力一直是老大，美的在做渠道扁平化、T+3这些，一直没看到成果，突然疫情来了，美的占有率哗一下就上去了，超过格力。当一些企业在埋头做事还没体现到报表时，我们往往忽略这些事情未来可能产生的重大影响。这些伟大的企业都是在特别特殊的时候拐上去的——平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞。
+**听众**：您讲到财富管理行业，能否具体展开讲一下投资逻辑和投资机会？
+**肖楠**：财富管理行业这个话题特别大，而且是分层的——顶级富豪的财富管理怎么管、普通中产阶级怎么做、中低收入人员怎么做，都有不同的公司和商业模式。我们最早是研究保险时发现一些有意思的事：某些保险公司一个保险员一单能签七八千的首期保费，有些公司平均一个业务员只有两三千的水平。我们花了很多时间调研特别厉害的销售和中等销售人员，发现同样是卖保险，背后的逻辑和机制差异超级大，而这些公司的结构设置、激励机制、文化又有巨大差异。去年发基金时也发现，有些渠道经理过来调研问的问题超级专业，有些渠道经理永远问下半年是涨是跌、明年是牛市还是熊市。同样在这个行业混的人，经营结果差距巨大。财富管理行业最大的逻辑在于财富分布超级不均匀，有些头部公司一口气拿掉行业增量的绝大部分，第二名只能拿到剩下部分的80%。在这种特别偏激、幂律分布的行业里，有可能诞生特别大的企业。遗憾的是，我们有些产品因为监管和法律规则的原因反而不能投类似标的，但未来合同设置更清晰时，可能会在这方面有所体现。
+**听众**：您讲到第二、第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
+**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营成功就说企业家特别厉害，就像不要因为一个基金经理过去业绩好就说他特别厉害。一定要把所有能归因到数据里客观指标的因素全部归因完，再特别谨慎地评价一些比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为企业家在所以公司就能值多少。我强调的一直是避免错误归因，避免因为对企业家认可而犯投资错误，一定要把底线风险搞好。我们一致同意这个东西不可被定价。这些比较虚的因素——技术进步、企业家精神——什么时候考虑？是在所有客观归因都尽量穷尽以后，可能某种程度上一些收益率的归因可以归到这里面。另外，只能在有限范围内做两两比较：两家公司做同样生意、同样产品，在这种限定条件下比较两个企业家的水平高低、理念先后，找你认可的那一家，仅此而已，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，要谨慎使用所谓企业家精神、伟大企业这些词，只在特别极端的时候，它可能是你某些信仰上的支持，但尽量不要去用。</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>199.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26252/4732</t>
+          <t>26252/8844</t>
         </is>
       </c>
     </row>
@@ -9251,6 +9245,61 @@
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>辩论会</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t># 辩论内容概述
+本次辩论赛围绕“拥有让人爱上自己的超能力是否美好”展开，正方为RUC棒辩论队，反方为对方辩友。正方主张超能力是爱的辅助，能让人直接达到真爱，并以月老、丘比特为例，认为超能力掌握在爱你的人手里更好；反方则认为超能力剥夺了对方的自由意志，是洗脑和占有，并以强奸类比，质疑其违背对方意志。双方就超能力与自由意志的冲突、爱的定义与标准等议题展开交锋，反方认为爱是玄学，科学无法解释，强调放手的爱；正方认为爱有标准，可以制定100%符合需求的人，并强调爱的过程需要相互尊重。最终正方获胜，获得4分钟小结时间。
+# 核心论点
+辩题为“拥有让人爱上自己的超能力是否美好”，正方为RUC棒辩论队，反方为对方辩友。双方围绕超能力与自由意志、爱的本质等展开交锋，正方主张超能力是爱的辅助，反方认为其剥夺自由意志。
+| 阵营 | 立论框架 | 核心论点 | 支撑论据 |
+| --- | --- | --- | --- |
+| 正方 | 爱是超能力，能让人直接达到真爱 | 超能力是爱的辅助，能让人直接达到真爱 | 月老、丘比特让有情人终成眷属；超能力掌握在爱你的人手里更好 |
+| 反方 | 爱是玄学，科学无法解释 | 超能力剥夺自由意志，是洗脑和占有 | 强奸类比；爱是玄学，科学无法解释 |
+| 正方 | 爱有标准，可以制定100%符合需求的人 | 超能力可能改变自己而非对方 | 根据对方标准制定100%符合需求的人；改变自己而非洗脑 |
+| 反方 | 应保留被爱者的选择空间 | 超能力导致爱变质 | 爱来得太容易，容易变质；放手的爱才是真爱 |
+# 争议焦点
+- **焦点**：超能力是否剥夺自由意志；正方：超能力是爱的辅助，能让人直接达到真爱，且机制更可能是改变自己而非洗脑；反方：超能力抹杀了对方的决定，是洗脑和占有，违背对方意志。
+- **焦点**：爱的本质是玄学还是有标准；正方：爱有标准，可以制定100%符合需求的人；反方：爱是玄学，科学无法解释，强调放手的爱。
+- **焦点**：超能力是否导致爱变质；正方：珍惜取决于认真程度，而非获得爱的难易；反方：超能力让爱来得太容易，容易变质。
+- **焦点**：超能力掌握在谁手里更好；正方：掌握在爱你的人手里比掌握在蒙眼的小孩子手里好；反方：应保留被爱者的选择空间，避免自私。
+# 环节交锋
+## 质询环节
+- 正方质询反方：正方问反方是否认为超能力是操控自由意志、像洗脑；反方回应称超能力剥夺了对方的决定，是占有而非爱。
+  &gt; “你方觉得我们这个超能力就是操控他的自由意志，有点像给他洗脑。”
+- 反方质询正方：反方以强奸类比，质疑超能力违背对方意志；正方回应称发生性关系由对方决定，但爱上与否与自由意志无关。
+  &gt; “强奸这件事情叫做违背妇女意志，强行发生性关系，而今天在面对情况当中，为什么是违背对方意志，强行介入亲密关系。”
+- 正方质询反方：正方提出超能力可能改变自己而非对方；反方质疑改变自己是否可能被接受。
+  &gt; “那能不能是我改变我自己。”
+- 反方质询正方：反方质疑超能力导致爱变质；正方反驳珍惜取决于认真程度，而非新鲜感。
+  &gt; “难道我们在恋爱过程当中珍不珍惜对方这件事情完全看我们之间的新鲜感？”
+## 自由辩论环节
+- 正方进攻：正方以月老、丘比特为例，认为超能力掌握在爱你的人手里更好；反方回应称月老让有情人终成眷属，而超能力可能拆散真爱。
+  &gt; “月老和丘比特他让有情人终成眷属。”
+- 反方进攻：反方提出放手的爱，正方认为放手不是爱；反方质疑正方定义伤害的标准。
+  &gt; “这些伤不伤害都是你定义的，你自己觉得自己跟他在一起不是伤害，别人跟他在一起是伤害。”
+- 正方进攻：正方提出超能力可能改变自己而非对方；反方质疑洗脑是否就是爱。
+  &gt; “洗脑就是爱吗？”
+- 反方进攻：反方质疑超能力导致爱变质；正方反驳珍惜取决于认真程度。
+  &gt; “我们最能够让爱保鲜的方式就是在恋爱过程当中相互忽略。”
+## 总结环节
+- 正方总结：正方指出反方预设了人在爱上不能有自由意志的前提，并强调超能力的机制更可能是改变自己而非洗脑。
+  &gt; “你方预设了一个前提，就是在爱或不爱这件事情上，人是不能有自由意志的。”
+- 反方总结：反方强调应保留被爱者的选择空间，避免自私。
+  &gt; “我们一定要保留一个希望，一定要保留一个被爱的那个人的选择空间。”
+# 结辩与评委点评
+- **正方结辩**：正方指出反方预设了人在爱上不能有自由意志的前提，并强调超能力的机制更可能是改变自己而非洗脑，且珍惜程度取决于认真对待感情的态度。正方认为超能力掌握在爱你的人手里更好，能避免遗憾。
+- **反方结辩**：反方强调应保留被爱者的选择空间，避免自私，并质疑超能力导致爱变质。反方认为爱是玄学，科学无法解释，放手的爱才是真爱。
+- **评委点评**：主持人宣布正方获胜，获得4分钟小结时间。</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>12403/2040</t>
         </is>
       </c>
     </row>
@@ -9604,6 +9653,49 @@
           <t>就医咨询</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t># 就诊概况
+患者为老年女性，因结肠癌术后多发转移，由家属代述就诊。患者于2023年9月因突然腹痛（疼了一晚上）确诊结肠癌并接受切除手术，术后完成8期化疗。复查发现肝转移，于去年9月行肝消融和乳腺结节切除，当时存在腹膜转移，肠切除时医生表示可能切得不是特别干净。消融和结节切除后继续化疗，但仅第一次检查，后续因肝功能不佳停用部分药物，中间停药3个月。3月底复查发现肝、肺、腹膜再次转移，4月份CT显示广泛转移。上个月肠镜显示无异常，但PET显示有转移，医生认为可能肠镜做得不好。本次就诊要解决的问题是：在多发转移情况下，除化疗和靶向治疗外是否有更有效的全身治疗方案，以及是否需要再做核磁等检查。
+# 病史与背景
+- **发病与确诊**：2023年9月因突然腹痛（疼了一晚上）就诊，确诊结肠癌并接受切除手术。
+- **既往肠胃情况**：多年来吃东西易中毒，如吃海鲜就上吐下泻，一直被认为肠胃比较弱。
+- **术后化疗**：术后完成8期化疗。
+- **肝转移与局部治疗**：复查发现肝转移，去年9月行肝消融和乳腺结节切除。
+- **腹膜转移**：当时存在腹膜转移，肠切除时医生表示可能切得不是特别干净。
+- **后续化疗与停药**：消融和结节切除后继续化疗，但仅第一次检查，后续因肝功能不佳停用部分药物，中间停药3个月。
+- **再次转移**：3月底复查发现肝、肺、腹膜再次转移，4月份CT显示广泛转移。
+- **肠镜与PET结果**：上个月肠镜显示无异常，但PET显示有转移，可能肠镜质量不佳。
+# 诊断与检查结果
+- **诊断结论**：结肠癌术后多发转移（肝、肺、腹膜），考虑为广泛性转移，需进一步明确基因突变情况以指导治疗。
+- **检查结果**：4月份CT显示广泛转移；上个月肠镜显示无异常，但PET显示有转移，医生认为可能肠镜做得不好。
+- **医生说明**：基因检测可通过组织、血液、尿液、唾液进行，其中组织检测阳性率高，但成本高；唾液检测也可用于基因检测。
+- **家属疑问**：家属询问除化疗和靶向治疗外是否有更有效手段，以及是否需要再做核磁；医生认为当前主要问题是全身系统治疗，而非局部介入。
+# 治疗方案与医嘱
+- **检查安排**：建议进行二次基因检测，以明确基因突变情况，指导后续靶向和免疫治疗。
+- **治疗方向**：当前治疗重点为全身系统治疗（化疗、靶向、免疫），而非局部介入；免疫加靶向的联合治疗可能协同增效。
+- **生活方式**：建议患者母亲调整状态，提升免疫力。
+- **用药说明**：提到四联康，用于肚子不好时，但患者未关注。
+| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
+| --- | --- | --- | --- | --- |
+| 四联康 | — | — | — | 用于肚子不好时，但患者未关注 |
+# 复诊与预警信号
+## 复诊与随访安排
+- **复查项目**：建议进行二次基因检测，以指导后续治疗。
+## 预警信号
+- ⚠️ 肝功能不佳，曾导致化疗药物停用。
+## 需要观察的变化
+- 监测肝功能变化，若肝功能不佳可能影响化疗药物使用。</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>7063/1313</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="9">
       <c r="A28" s="6" t="inlineStr">
@@ -9759,6 +9851,49 @@
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>产品发布</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t># 产品概况
+海尔洗衣机创新发布会于海尔洗衣机用户研发中心举行，主讲人发布了专为中国家庭打造的洗干集成新物种——迭代H2。产品以“洗干集成新物种”为定位，针对中国80%用户将洗烘套装叠放于阳台的使用习惯，采用一体集成机身，解决叠放带来的震动等安全隐患，高度降至167厘米，超薄机身可嵌入60厘米标准橱柜，全平不突出。H2以屏幕为核心，可操控洗涤、烘干和护理等多种模式，搭载灵犀洗烘联动、原创双擎热泵技术、3D透视烘干、精华洗2.0、空净过滤系统及三台变频电机等创新技术，旨在让用户告别晾晒，享受整洁有序的新阳台生活。
+# 市场定位与目标用户
+目标人群为中国家庭，尤其是追求整洁有序新阳台的年轻人及养宠、有宝宝的家庭。典型使用场景为客阳一体空间，用户在此休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间。针对中国80%用户将洗烘套装叠放于阳台带来的屏幕过高、开门方向相反、水盒太高太沉等不便，H2以一体集成机身、同向开门、无水盒设计等解决痛点。原文未提及同类产品或上代产品的直接对比。
+# 核心卖点与技术参数
+## 一体集成设计
+- **一体集成机身**：专为客阳一体空间设计，解决洗烘套叠放带来的震动等安全隐患，高度降为167厘米，不用踮脚即可操作。
+- **超薄平嵌**：超薄机身完美嵌入60厘米标准橱柜，全平不突出，让阳台更美观整洁。
+- **同向开门**：尊重使用习惯，取放衣物流畅自如。
+- **无水盒设计**：无需手动倒水。
+## 智慧互联
+- **灵犀洗烘联动**：H2独有的洗烘联动实现数据共享，洗涤结束前上桶提前15分钟主动预热，缩短烘干时长。
+- **智慧大脑**：以屏幕为核心，可全面操控洗涤、烘干和护理等多种模式，利用中枢神经式智能网络让上下桶默契配合。
+## 烘干技术
+- **原创双擎热泵技术**：大件烘干不缠绕。
+- **3D透视烘干**：首次引入行业领先黑科技，羽绒服、水洗被可一次烘透，免去二次晾晒。
+## 洗涤技术
+- **精华洗2.0**：激活洗衣液，39分钟洗净一周衣物。
+- **新鲜净水漂洗**：减少洗衣液残留，对残留泡沫敏感人群友好。
+## 健康与静音
+- **空净过滤系统**：去除衣物线屑和毛絮，适合养宠家庭，洗衣无残留、干衣无毛絮。
+- **三台变频电机**：洗涤、甩干、烘干全过程噪音低，夜晚也能安静洗。
+| 维度 | 本产品 | 上代/竞品 | 提升 |
+| --- | --- | --- | --- |
+| 一体集成设计 | 一体集成机身，高度167厘米，超薄嵌入60厘米标准橱柜，全平不突出，同向开门，无水盒设计 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决震动安全隐患，操作更便捷，阳台更美观整洁 |
+| 智慧互联 | 灵犀洗烘联动，洗涤结束前上桶提前15分钟主动预热 | 洗烘套装貌合神离，无联动 | 数据共享，烘干与洗涤无缝连接，缩短烘干时长 |
+| 烘干技术 | 原创双擎热泵技术，3D透视烘干，大件不缠绕，羽绒服、水洗被一次烘透 | 未提及 | 免去二次晾晒 |
+| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗减少残留 | 未提及 | 洗衣更高效，减少洗衣液残留 |
+| 健康与静音 | 空净过滤系统去除线屑毛絮，三台变频电机低噪音 | 未提及 | 洗衣无残留、干衣无毛絮，安静陪伴 |
+# 定价与发售信息
+10kg 3D透视烘干款定价12998元，10kg 净净双擎热泵款定价10998元。主讲人表示“对这款平嵌超薄产品拿出了诚意满满的定价”。原文未提及发售时间、购买渠道与预售政策。</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7311/1505</t>
         </is>
       </c>
     </row>
@@ -9958,6 +10093,96 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t># 全文摘要
+中共巢湖市银屏镇白母山村芦塘支部召开党员大会改选支部委员会，支部共有正式党员8名，因病请假1名，实到7名，符合法定人数；银屏镇党委组织委员钱小丽到会指导并就换届选举提出三点意见。会议围绕上届支委会工作报告、通过选举办法与候选人名单、候选人竞职演说、无记名投票选举新一届支部委员及书记、支委分工等议程展开。经投票，卢艳娇、辛东升、杜军强当选新一届支部委员会委员，卢艳娇当选支部书记，辛东升负责组织宣传、杜军强负责纪检，选举结果以报镇党委批准为准；上届工作报告获鼓掌通过。关键数字：支部正式党员8名、实到7名（达应到会4/5）、发出并收回选票7张、卢艳娇与杜军强各得6票、党费收缴2640元。
+# 分段速览
+## 00:00:13–00:02:41 大会开幕与镇党委讲话
+会议主持人宣布中共巢湖市银屏镇白母山村芦塘支部党员大会开幕，说明支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。全体起立奏国歌后，镇党委组织委员钱小丽讲话，代表镇党委就换届选举提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律，并希望新一届班子加强学习、发挥战斗堡垒作用。
+## 00:02:41–00:05:12 上届支部委员会工作报告
+主持人代表上届支部委员会作三年工作报告，涵盖思想政治建设与理论学习、党支部建设、主题教育活动、党务公开、党风党纪教育五个方面，并指出存在问题：党建工作制度不够完善、党员主体意识尚需提高、党支部对党员教育管理监督不够深入。报告经与会党员讨论后鼓掌通过。
+## 00:05:12–00:10:43 通过选举办法、候选人名单与工作人员名单
+大会依次进行三项议程。杜军晓宣读党员大会选举办法草案，规定选举支部委员3名、候选人4名，差额不少于应选名额20%，采用无记名投票，先差额选委员再等额选书记，经表决一致通过。随后宣读镇党委批复，确定委员候选人卢燕娇、辛东升、杜军强、秦磊，书记候选人卢艳娇，鼓掌通过。最后通过监票人贾淑玲、计票人黄婷丽和刘彩云的名单。
+## 00:10:43–00:14:45 候选人竞职演说
+四位候选人依次发表竞职演说。卢艳娇介绍个人情况并承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强表示可发挥村委会工作优势担当桥梁纽带；辛东升承诺群众有困难随叫随到、严格要求自己、完成上级任务；秦磊阐述自身责任心与思想觉悟方面的有利条件。
+## 00:14:45–00:21:17 大会选举新一届支部委员会
+大会清点人数确认实到有选举权党员7名，达到应到会4/5要求。监票人检查并封好票箱后分发选票，主持人说明填写方法与注意事项。投票后清点，发出选票7张、收回7张，选举有效。计票结果卢艳娇6票、杜军强6票、秦磊2票，卢艳娇、辛东升、杜军强当选为新一届支部委员会委员。
+## 00:21:17–00:28:42 第一次支委会选举书记及分工
+新当选委员召开第一次支部委员会全体会议，通过选举办法草案，确定书记候选人建议名单为卢艳娇，通过辛东升担任监票人和计票人。发出并收回选票3张，卢艳娇得3票当选为党支部书记。随后进行委员分工，辛东升负责组织宣传工作，杜军强负责纪检工作。
+## 00:28:42–00:29:56 宣布结果与新当选代表发言
+主持人向大会宣布卢艳娇当选为党支部书记，最终结果以报镇党委批准为准。新当选支委代表发言，承诺抓好支部学习工作、制度建设工作并完善基层党组织建设，争创学习型、制度型、服务型支部。大会完成各项任务后奏国际歌，换届选举大会圆满结束。
+# 要点梳理
+## 会议筹备与开幕
+- 支部共有党员8名，其中正式党员8名，有选举权；因病请假1名，实到会有选举权党员7名，符合法定人数，可以开会。
+- 银屏镇党委组织委员钱小丽应邀到会指导。
+- 主持人宣布换届选举党员大会开始，全体起立奏国歌。
+- 钱小丽代表镇党委就换届选举工作提三点意见：充分认识大会重要意义；正确行使选举权，严格把握选举要求；服从大局，严格遵守选举纪律。
+## 上届支部委员会工作报告
+- 上届支部委员会报告三年工作，涵盖思想政治建设和理论学习、党支部建设、主题教育活动、党务公开、党风党纪教育五个方面。
+- 党支部严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度。
+- 三年间新发展党员1名，按规定收缴党费2640元上交上级党组织。
+- 认真开展"两学一做"学习教育常态化制度化和"讲严立"专题警示教育活动。
+- 将年度工作计划、党风廉政建设、党费收缴等内容通过党内会议、公开栏等形式公开。
+- 报告指出存在问题：党建工作制度不够完善；党员主体意识尚需进一步提高，个别党员干部围绕中心服务大局的意识不强；党支部对党员的教育管理监督不够深入。
+- 与会党员对报告表示满意，鼓掌通过。
+## 通过大会选举办法
+- 杜军晓宣读党员大会选举办法草案，规定大会选举支部委员会委员3名，候选人4名，差额不少于应选名额20%。
+- 选举采用无记名投票方式，先差额选举支部委员会委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布结果。
+- 参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举。
+- 收回选票数等于或少于发出选票数选举有效，多于发出选票数选举无效。
+- 候选人得到赞成票数超过应到会选举人数的半数方可当选；得票超过半数候选人多于应选名额时以得票多少为序取足应选名额。
+- 选举设监票人1名，经大会表决通过；设选举工作人员2名，由会议主持人指定；提名作为支部委员候选人的不能担任监票人和工作人员。
+- 与会党员表决一致通过选举办法草案。
+## 通过支委候选人名单
+- 杜军晓宣读银屏镇党委批复，同意新一届支部委员会委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢艳娇。
+- 批复明确委员实行差额选举，差额1人，书记实行等额选举，选举结果报镇党委批准；批复日期为2019年10月12日。
+- 与会党员鼓掌通过候选人名单。
+## 通过选举工作人员名单
+- 提议贾淑玲担任监票人，经表决一致通过。
+- 宣布计票人员名单：黄婷丽、刘彩云。
+## 候选人竞职演说
+- **卢艳娇**：1993年9月出生，2014年4月加入中国共产党；承诺进一步加强支部建设，落实"三会一课"、组织生活会和民主评议党员等基本制度；推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领和帮扶帮带作用；抓好各项民生工程落实，把群众利益作为首要职责。
+- **杜军强**：从事村委会工作，表示农村党支部是基层党组织与党员群众之间的桥梁纽带，如当选可更好担当纽带角色，为党员和群众服务。
+- **辛东升**：承诺群众有困难随叫随到；严格要求自己做合格党员干部，不该吃的饭不吃、不该拿的钱不拿、不该做的事不做；圆满完成上级党组织分配的各项任务。
+- **秦磊**：自述有较强责任心，能认真参加支部理论学习、不折不扣完成组织交给的任务；有较高思想觉悟，积极向群众宣传并带头遵守；承诺配合上级各项工作，全体党员团结一心，不计较个人得失。
+## 大会选举新一届支部委员会
+- 应到会有选举权党员8名，因病请假1名，实到7名，达到应到会有选举权党员人数的4/5，可以进行选举。
+- 监票人员检查并封好票箱，计票人员领取并分发选票。
+- 主持人说明填写选票方法：赞成在候选人姓名上方空格画圈，不赞成画叉，弃权不画符号；另选他人在候选人后面空格写姓名并在上方画圈，不画圈无效；每张选票所选人数等于或少于应选人数为有效票，多于应选人数为无效票；填写一律用钢笔。
+- 投票顺序为监票人员、计票人员先投票，然后全体党员依次投票。
+- 实到会有选举权党员7名，发出选票7张，收回选票7张，选举有效。
+- 计票结果：卢艳娇6票，杜军强6票，秦磊2票。
+- 根据大会选举办法规定，卢艳娇、辛东升、杜军强当选为新一届支部委员会委员。
+## 第一次支部委员会全体会议
+- 新当选支部委员召开第一次全体会议，议程三项：宣读选举办法草案、选举支部书记、对支委会委员进行分工。
+- 选举办法规定：支部书记采用等额选举；实到会委员必须超过应到会委员的4/5方可进行选举；候选人得到赞成票超过实到会委员半数当选。
+- 书记候选人建议名单为卢艳娇，主持人介绍其工作认真负责，上届支委会在其带领下各项工作取得较好成绩，建议继续担任支部书记，鼓掌通过。
+- 提议辛东升担任监票人和计票人，表决一致通过。
+- 发出选票3张，收回选票3张，卢艳娇得3票，当选为新一届党支部书记。
+- 分工安排：辛东升负责组织宣传工作，杜军强负责纪检工作。
+## 宣布选举结果及新当选代表发言
+- 主持人宣布卢艳娇当选为巢湖市银屏镇白母山村芦塘党支部书记，最终结果以报镇党委批准为准。
+- 新当选支委代表发言，承诺抓好支部学习工作，争创学习型支部，认真组织开展"不忘初心、牢记使命"主题教育；抓好支部制度建设工作，争创制度型支部；完善基层党组织建设，争创服务型支部，严格按照《中国共产党支部工作条例（试行）》加强支部建设。
+- 大会完成各项任务，全体起立奏国际歌，换届选举大会圆满结束。
+## 结论与决定
+- 通过上届支部委员会工作报告。
+- 通过党员大会选举办法草案。
+- 通过支委候选人名单：卢燕娇、辛东升、杜军强、秦磊。
+- 通过监票人贾淑玲、计票人黄婷丽、刘彩云名单。
+- 卢艳娇、辛东升、杜军强当选为新一届支部委员会委员。
+- 卢艳娇当选为新一届党支部书记，选举结果以报镇党委批准为准。
+- 辛东升负责组织宣传工作，杜军强负责纪检工作。</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8414/3992</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="13.5" customHeight="1" s="9">
       <c r="A30" s="6" t="inlineStr">
@@ -10087,6 +10312,129 @@
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>政府报告</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t># 报告概况
+国务院总理代表国务院作政府工作报告，回顾2023年工作，提出2024年经济社会发展总体要求、主要预期目标和政府工作任务，请全国人大代表审议，并请全国政协委员提出意见。报告指出，2023年是全面贯彻党的二十大精神的开局之年，面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务，全年经济社会发展主要目标任务圆满完成，高质量发展扎实推进，社会大局保持稳定。2024年是中华人民共和国成立75周年，是实现“十四五”规划目标任务的关键一年，报告坚持稳中求进工作总基调，部署大力推进现代化产业体系建设、深入实施科教兴国战略、着力扩大国内需求、坚定不移深化改革、扩大高水平对外开放、更好统筹发展和安全、扎实推进乡村全面振兴、推动城乡融合和区域协调发展、加强生态文明建设、切实保障和改善民生等十个方面政府工作任务。
+# 核心政策
+## 2024年经济社会发展总体要求
+- **总体要求**：坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，加快构建新发展格局，着力推动高质量发展，全面深化改革开放，推动高水平科技自立自强，加大宏观调控力度，统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全。
+- **政策基调**：坚持稳中求进、以进促稳、先立后破，多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施，在转方式、调结构、提质量、增效益上积极进取，强化宏观政策逆周期和跨周期调节。
+- **宏观政策取向一致性**：围绕发展大局加强政策协调配合，把非经济性政策纳入宏观政策取向一致性评估，确保同向发力、形成合力；涉企政策要注重与市场沟通，回应企业关切，营造稳定、透明、可预期的政策环境。
+## 2024年主要预期目标
+- **经济增长**：国内生产总值增长**5%左右**。
+- **就业**：城镇新增就业**1120万人**，城镇调查失业率**5.5%左右**。
+- **物价**：居民消费价格涨幅**3%左右**。
+- **收入与外贸**：居民收入增长和经济增长同步，国际收支保持基本平衡。
+- **粮食安全**：粮食产量**1.3万亿斤以上**。
+- **能耗与生态**：单位国内生产总值能耗降低**2.5%左右**，生态环境质量持续改善。
+## 财政政策
+- **总体取向**：积极的财政政策要适度加力、提质增效，大力优化支出结构，强化国家重大战略任务和基本民生财力保障。
+- **赤字与支出**：赤字率拟按**3%**安排，一般公共预算支出规模**28.5万亿元**。
+- **地方政府专项债券**：拟安排地方政府专项债券**3.9万亿元**。
+- **超长期特别国债**：为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，今年先发行**10000亿元**。
+- **财力下沉**：中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜；省级财政要推动财力下沉，兜牢基层`三保`底线。
+- **过紧日子**：各级政府要习惯过紧日子，切实把财政资金用在刀刃上、用出实效。
+## 货币政策
+- **总体取向**：稳健的货币政策要灵活适度、精准有效，保持流动性合理充裕。
+- **融资成本**：社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配，促进社会综合融资成本稳中有降。
+- **资本市场与汇率**：增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。
+## 现代化产业体系建设
+- **产业链优化升级**：实施`制造业重点产业链高质量发展`行动，着力补齐短板、拉长长板、锻造新板，推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的`中国制造`品牌。
+- **战略性新兴产业**：促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
+- **数字经济**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展`人工智能+`行动，实施`制造业数字化转型`行动，大力推动数据开发开放和流通使用。
+## 科教兴国战略
+- **教育强国**：制定实施`教育强国建设规划纲要`，落实立德树人根本任务，开展`基础教育扩优提质`行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
+- **科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发，强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作。
+- **人才政策**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
+## 扩大国内需求
+- **促进消费**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施`数字消费`、`绿色消费`、`健康消费`促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质。
+- **扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳，加强民生等经济社会薄弱领域，加快实施`十四五`规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
+## 深化改革
+- **激发经营主体活力**：不断完善落实`两个毫不动摇`的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施`国有企业改革深化提升`行动，全面落实促进民营经济发展壮大的意见及配套举措，实施`降低物流成本`行动，健全防范化解拖欠企业账款长效机制。
+- **全国统一大市场**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
+- **财税金融改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
+## 高水平对外开放
+- **外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
+- **吸引外资**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施`自贸试验区提升`战略，打造对外开放新高地。
+- **共建一带一路**：抓好支持高质量共建`一带一路`八项行动落实落地，稳步推进重大项目合作，实施一批`小而美`民生项目，加快建设西部陆海新通道。
+- **多双边合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
+## 防范化解重点领域风险
+- **房地产风险**：优化房地产政策，促进房地产市场平稳健康发展；加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求。
+- **地方债务风险**：统筹好地方债务风险化解和稳定发展，进一步落实`一揽子化债方案`，稳妥推进一些地方的中小金融机构风险处置。
+- **风险防控长效机制**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
+- **重点领域安全**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
+## 乡村全面振兴
+- **粮食稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平；各地区都要扛起保障国家粮食安全责任。
+- **巩固脱贫成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度。
+- **农村改革**：启动第二轮土地承包到期后再延长**30年**整省试点，促进农民增收，壮大乡村富民产业。
+- **乡村建设**：深入实施`乡村建设`行动，持续改善农村人居环境，建设宜居宜业和美乡村；学习运用`千村示范、万村整治`工程经验，推动乡村全面振兴不断取得实质性进展、阶段性成果。
+## 城乡融合与区域协调发展
+- **新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
+- **区域重大战略**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用；持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
+## 生态文明建设
+- **生态环境治理**：深入实施`空气质量持续改善`行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好`三北`工程三大标志性战役，完善生态产品价值实现机制。
+- **绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
+- **碳达峰碳中和**：扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
+## 保障和改善民生
+- **稳就业促增收**：突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过**1170万人**，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
+- **医疗卫生**：居民医保人均财政补助标准提高**30元**；深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展`健康中国`行动和爱国卫生运动。
+- **社会保障**：城乡居民基础养老金月最低标准提高**20元**，继续提高退休人员基本养老金；加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系。
+- **文化生活**：创新实施`文化惠民`工程，大力发展文化产业，推动全民健身活动广泛开展。
+- **社会治理**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；坚持和发展新时代`枫桥经验`，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
+# 重点工作
+## 大力推进现代化产业体系建设，加快发展新质生产力
+- **推动产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌。
+- **促进战略性新兴产业融合集群发展**：巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
+- **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展“人工智能+”行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
+## 深入实施科教兴国战略，强化高质量发展的基础支撑
+- **加强高质量教育体系建设**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务，开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
+- **加快推动高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发；强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作，营造具有全球竞争力的开放创新生态。
+- **全方位培养用好人才**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
+## 着力扩大国内需求，推动经济实现良性循环
+- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
+- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳，加强民生等经济社会薄弱领域，加快实施“十四五”规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
+## 坚定不移深化改革，增强发展内生动力
+- **激发各类经营主体活力**：不断完善落实“两个毫不动摇”的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投。
+- **加快全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
+- **推进财税、金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
+## 扩大高水平对外开放，促进互利共赢
+- **推动外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
+- **加大吸引外资力度**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施自贸试验区提升战略，打造对外开放新高地。
+- **推动高质量共建“一带一路”走深走实**：抓好支持高质量共建“一带一路”八项行动落实落地，稳步推进重大项目合作，实施一批“小而美”民生项目，加快建设西部陆海新通道。
+- **深化多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
+## 更好统筹发展和安全，有效防范化解重点领域风险
+- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
+- **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
+- **加强重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
+## 坚持不懈抓好“三农”工作，扎实推进乡村全面振兴
+- **加强粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平，各地区都要扛起保障国家粮食安全责任。
+&gt; 我们这样一个人口大国，必须始终把饭碗牢牢端在自己手上。
+- **毫不放松巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
+- **稳步推进农村改革发展**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业；深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
+## 推动城乡融合和区域协调发展，大力优化经济布局
+- **积极推进新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
+- **提高区域协调发展水平**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
+## 加强生态文明建设，推进绿色低碳发展
+- **推动生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好“三北”工程三大标志性战役，完善生态产品价值实现机制。
+- **大力发展绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
+- **积极稳妥推进碳达峰碳中和**：扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
+## 切实保障和改善民生，加强和创新社会治理
+- **多措并举稳就业促增收**：突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
+- **提高医疗卫生服务能力**：居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展健康中国行动和爱国卫生运动。
+- **加强社会保障**：城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金；加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢。
+- **丰富人民群众精神文化生活**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。
+- **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代“枫桥经验”，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9903/8267</t>
         </is>
       </c>
     </row>
@@ -10918,6 +11266,97 @@
           <t>沟通交流会</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t># 沟通背景与目的
+杭州医学院检验医学院、生物工程学院举办专场招生直播，由学院党委书记、副院长宋宝峰副教授主讲，面向考生及家长介绍医学技术专业硕士点的招生情况与培养特色。沟通旨在帮助广大考生全面了解2026年研究生招生情况，围绕学位点基本情况、学科建设与优势、主要研究方向、师资队伍、硕士培养与毕业去向、2026年招考计划及复试安排等主题展开，并现场解答考生关于就业前景、初试科目、跨专业报考等疑问。整体基调为积极推介，宋宝峰强调该学位点学科竞争力强、就业面广，并欢迎考生报考。
+# 核心信息与数据
+## 学位点基本情况
+- **学位点获批**：杭州医学院医学技术专业硕士点于2024年获批，为新的学位点。
+- **共建学院**：由检验医学院、生物工程学院（合署办公）牵头，医学影像学院、康复学院、信息工程学院共建，共5个学院承担培养工作。
+- **专业方向**：聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个主要专业方向，其中检验技术细分为医检和卫检两个方向。
+- **2025年招生**：录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
+## 学科建设与优势
+- **学科层次**：医学技术于2023年获批省一流学科B类。
+- **科研项目与经费**：近五年获国家级基金项目19项、省鉴定领先项目1项，纵向科研经费1300万，横向合作课题经费2200多万。
+- **科研获奖**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
+- **课程与专业建设**：建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
+- **省级科研平台**：建有省生物标志物与器官诊断转化重点实验室、检验诊断关键技术研究室、康复模块和机器人国际联合实验室、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、浙江省神经系统疾病数字化装备研发重点实验室等。
+- **体外诊断领域优势**：疫情期间与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册。
+- **医学影像技术优势**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向。
+- **康复治疗优势**：依托省人民医院康复医学科，为省内综合医院中建科最早、人才最齐、技术最先进、设备最先进、社会效益最佳的康复医学科之一。
+- **智能医学工程优势**：聚焦阿尔茨海默病智能预警生物标志物（数字生物标志物），居国际领跑水平。
+## 主要研究方向
+- **医学检验技术（负责人吕建新教授）**：聚焦重大疾病新型生物标志物筛选及机制研究、新发突发传染病新型生物标志物筛选及致病机制研究、重大疾病体外诊断检测技术研究、新型药物系统体内治疗易复发难治愈疾病研究、神经免疫与再生研究。
+- **卫生检验检疫（负责人金大志研究员）**：聚焦新发突发传染病病原体检测检验新技术方法开发，特别是艰难梭菌致病机制、耐药机制、基因组进化及小分子药物开发，以及卫生检验技术研究。
+- **医学影像技术（负责人徐秀芳教授）**：研究多参数MRI有效指标、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位。
+- **康复治疗（负责人倪湘明教授，附属人民医院）**：研究康复技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病机制及临床研究。
+- **智能医学工程（负责人李海教授）**：聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病（阿尔茨海默病、帕金森病、抑郁症、自闭症等）智能诊断及数字方向。
+## 师资队伍与领军人物
+- **师资总体情况**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，正高35人，博士46人。
+- **人才称号**：教育部医学技术类专业技能教授委员会委员、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。
+- **吕建新教授（学位点负责人）**：博士，国家百千万人才工程人选、国家行业企业专家、省万人计划领军人才，教育部医学技术类专业教学指导委员会委员，主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表高水平论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项。
+- **徐秀芳教授**：浙江省151人才第三层次、省高校中青年学科带头人，研究生院院长兼医学影像学院院长，国家一流本科专业建设点（医学影像技术）负责人，近三年以通讯作者或第一作者发表多篇高水平论文。
+- **叶祥明教授**：省人民医院主任医师、二级教授、博导，省卫生领军人才，国家区域医疗中心浙江省重点培育专科康复医学学科带头人，主持国家级课题3项、省重大课题2项，发表SCI论文98篇。
+- **金大志研究员**：博士、硕导，美国华盛顿大学博士后，省创新人才、省卫生创新人才，主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划、省自然基金重点项目、省部共建重大项目共25项，发表SCI论文50多篇，获省科技进步奖二等奖1项、三等奖1项。
+- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士，早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长，研制全生命周期中医治疗及康复医疗体系设备3套。
+## 硕士培养与毕业去向
+- **培养目标**：面向健康中国发展需要，紧密服务区域行业产业发展，培养熟练掌握医学技术领域专业知识技能、具有良好创新实践能力的高层次应用型人才。
+- **培养方式与学制**：采用教学、专业实践及学位论文相结合方式；全日制专业学位学制三年，最长不超过五年。
+- **学分要求**：毕业前学业课程不少于24学分，其中专业必修课≥12学分，专业选修课≥6学分（可选智慧医疗、中医康复治疗学、生物信息学等）。
+- **培养环节**：第二学期开题，第三、第四学期（研二）完成过程性考核，研一第二学期进行学位论文答辩。
+- **医院就业方向**：检验方向可进入检验科、输血科、病理科；影像技术方向可进入放射科、超声科；康复治疗方向可进入康复医学科、骨科、神经科、运动医学科等。
+- **公共卫生就业方向**：卫检方向可进入疾病预防控制中心（CDC），参与传染病防控、慢性病防治等公共卫生工作。
+- **企业就业方向**：医药企业与生物技术公司（研发、生产、市场销售、质量管理与法规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）。
+- **其他就业方向**：药监局、卫健委、海关（医疗器械监管、卫生政策制定、口岸卫生检疫），高校、研究所继续深造（读博或从事研究）。
+- **就业实例**：东阳市疾控中心招聘检验方向微生物检验、理化检验岗位，要求硕士及以上。
+## 2026年招考计划
+- **计划招生**：2026年计划招生34人，实际以教育部正式下达人数为准。
+- **初试科目**：思想政治理论、英语为统考，专业课按方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）。
+- **检验综合考试内容**：分子生物学检验占40%、生物化学检验占30%、微生物学检验占30%。
+- **专业课考试形式**：满分300分，考试时长180分钟。
+- **复试占比**：初试占60%，复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%。
+- **复试形式**：目前以线下为主，具体以学校复试录取办法为准，可参考2025年复试办法。
+- **信息渠道**：杭州医学院研究生招生网（研究生招生.杭州医学院.edu.cn），研究生教育微信公众号。
+## 考生问答要点
+- **就业前景**：就业面广，可继续深造读博，或进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等，研究生学历具有核心竞争力。
+- **英语难度**：研究生入学考试英语难度介于四级和六级之间。
+- **跨专业报考**：允许非本专业考生跨专业报考医学技术专业，可提高录取概率。
+- **校区与交通**：学校有三个校区，主校区在市中心黄龙校区，交通便利。
+- **学科竞赛**：学校重视学科竞赛，研究生在竞赛中取得好成绩，以赛促学、以赛促教、以赛促改。
+# 各方立场与诉求
+- **主持人**：代表后台考生提出就业前景关注，询问在当前经济形势下医学技术专业研究生毕业后的就业前景。
+- **宋宝峰**：回应就业前景非常好，强调培养的是高层次应用型医学技术人才，就业面宽广，可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等单位，研究生学历具有核心竞争力，呼吁考生不必过度担心和焦虑。
+- **主持人**：代考生询问硕士研究生入学考试初试科目有哪些，以及如何利用暑期时间备考。
+- **宋宝峰**：回应初试共三门，思想政治理论和英语为统考，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；英语难度介于四级和六级之间，建议暑期重点备考，专业课可关注学校研究生招生网和研究生教育微信公众号获取考试大纲与参考教材。
+- **主持人**：代考生提出跨专业报考的疑问，询问非本专业考生能否报考医学技术专业。
+- **宋宝峰**：明确回应允许非本专业考生跨专业报考医学技术专业，鼓励跨学科跨专业报考，并指出跨专业报考被录取的概率会大大提高。
+- **主持人**：代考生询问学校交通条件及研究生能否参加学科竞赛。
+- **宋宝峰**：回应学校有三个校区，主校区在市中心黄龙校区，交通便利；学校重视学科竞赛，研究生在竞赛中取得好成绩，通过以赛促学、以赛促教、以赛促改提高教学质量与人才培养水平。
+# 达成共识
+- **2026年招生计划**：计划招生34人，实际以教育部正式下达人数为准。
+- **初试科目**：思想政治理论、英语为统考科目，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）。
+- **复试安排**：初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%，复试形式以线下为主。
+- **跨专业报考**：允许非本专业考生跨专业报考医学技术专业。
+# 待协调事项与后续
+## 待协调事项
+- **2026年实际招生人数**：以教育部正式下达为准，当前计划招生34人仅供参考
+- **复试具体形式与内容**：以学校复试录取办法为准，目前可参考2025年复试办法
+## 后续安排与参与方式
+- **直播回看**：本场直播结束后24小时内上传至B站，可随时搜索观看
+- **招生信息渠道**：关注杭州医学院研究生招生网（研究生招生·杭州医学院·教育·CN）及杭州医学院研究生教育微信公众号，可查询考试方向、考试大纲、参考教材与书籍
+- **初试备考**：暑期为关键备考期，英语难度介于四级和六级之间，建议以研究生考试英语真题为参照；思想政治理论需与时俱进学习
+- **报考咨询**：持续关注杭州医学院官网获取更多报考信息</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23026/4657</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="13.5" customHeight="1" s="9">
       <c r="A32" s="6" t="inlineStr">
@@ -11469,6 +11908,73 @@
           <t>课堂记录</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t># 课程概况
+本次课程为历史小论文写作专题课，由老师主讲、学生参与讨论。课程围绕小论文写作的核心要点展开，强调观点必须明确、论证一般写两到三条、结构需清晰（可按时间顺序或国内外等逻辑罗列）、结尾需升华观点。课堂重点讲解了自命题类、观点提示类、图表信息类等题型的解题方法：自命题类需按审题、读材料、列事实、控制时间的步骤进行；观点提示类需选择核心观点并明确表述，不能照抄材料；图表信息类需快速提取关键信息并分析关系。通过武汉长江大桥、历史材料观点评析等例题进行实践指导，学生结合四大发明、丝绸之路等史实进行论证练习。
+# 核心知识点梳理
+## 小论文写作核心要求
+- **观点明确**：观点必须亮出来，不能只是简单陈述形式或“几个方面加个名词”，要具有凝聚力。
+- **论证条数**：论证一般写两到三条，不宜太少（无法支撑论点）也不宜太多。
+- **结构清晰**：可通过序号或直接列条呈现，逻辑要清晰，可按时间脉络（如先秦、宋明、明清）或国内外、内外等维度罗列。
+- **结尾升华**：最后论述要升华观点，不能简单把观点抄一遍。
+## 自命题类解题方法
+- **审题**：先慢审题，看要求，注意“小红帽”要求及形成标准，明确是否限定用世界史知识或特定范围。
+- **读材料**：先大概看材料抓主要信息，再细看材料之间的关系。
+- **列事实**：先在草稿上写好题目，再罗列与材料相关的事实，不要直接写在答题卡上，避免写错又乱。
+- **控制时间**：注意时间控制，最后进行升华论述。
+## 观点提示类解题方法
+- **选择核心观点**：从材料给出的观点中选择一个核心观点，明确表述“我认为什么观点是正确的或错误的”。
+- **不能照抄**：不能照抄材料观点，需有自己的判断，在论点中详细表述。
+- **角度选择**：可用时间顺序或国内外等角度组织论述。
+- **结尾升华**：最后简单总结观点并进行升华。
+## 例题分析：武汉长江大桥
+- **材料背景**：涉及新中国成立、改革开放等背景，对澳门有重要作用。
+- **时间顺序**：应先写对内改革，再写对外开放，按时间顺序排列。
+- **审题要求**：需明确具体时间与事件，不能笼统，要求较高。
+## 例题分析：历史材料观点评析
+- **材料结构**：材料包含四个观点，涉及国民对本国历史应略有所知、了解本国利益、理性看待历史（不偏激民族主义、不将一切推于古人）、国家发展等。
+- **学生作答**：学生选择第二条观点进行评析，结合中华文化优越性、丝绸之路、四大发明对欧洲贡献等史实论证。
+- **教师点评**：需结合写作时代背景（1940年抗战时期），说明为何在此时期写此内容，不能只罗列史实。
+## 图表信息类解题方法
+- **快速提取**：迅速看图表题头、横向纵向信息，注意信息之间的关系变化。
+- **提取有效信息**：提取有效信息后再进行分析，结合材料与实践关系进行论述。
+- **例题说明**：涉及中国历代领导等级变化问题，可结合儒家思想、社会状态（如唐朝国力强盛但民德评价、宋明时期民德较高等）分析。
+# 课堂互动与答疑
+**学生**：武汉长江大桥这道题，我写的背景部分把对内改革和对外开放并列了，这样处理可以吗？
+**教师**：不行，要按时间顺序来写，先写对内改革，再写对外开放，不能并列。你写的内容要有重大国家利益支撑，审题时还要注意题目要求用的是世界史还是中国史知识，别搞错范围。
+**学生**：观点提示类题目里，材料给了四个观点，我选了第二条来评析，这样选可以吗？
+**教师**：可以，你选的第二条还可以。但要注意评析时不能照抄材料观点，要结合具体史实论证，比如四大发明对欧洲科技发展的影响、丝绸之路的经济文化交流等。还要说明为什么作者在1940年抗战时期写这个观点，要联系时代背景。
+**学生**：图表信息类题目，比如那个历代民德变化的图，我写的是整体变化趋势，这样写行不行？
+**教师**：整体写也行，但你要能解释清楚各时期高低变化的原因。比如唐朝国力强盛但民德评价不高，宋朝民德繁盛，你要结合社会状态、儒家思想影响来分析，不能只罗列现象。
+# 课后任务与学习建议
+## 课堂练习
+- **自命题类（武汉长江大桥）**：审题后读材料，抓新中国成立、改革开放等背景信息；按时间顺序先写对内改革、再写对外开放，罗列与材料相关的事实后再成文。
+- **观点提示类（历史材料观点评析）**：材料含四个观点（国民应略知本国历史、应敬畏祖国意志、理性看待历史不偏激、国家方能继续发展）；任选两个观点评析，不能重复材料观点，需结合四大发明、丝绸之路等史实论证并作出自己的判断。
+- **图表信息类（历代民德等级变化）**：快速看题头及横向纵向信息，注意关系变化；可写春秋、东汉、宋明等时期民德变化，结合儒学思想、社会状态分析，如唐朝国力强盛但民德较高需推论与制度改善的关系。
+- **图表信息类（中外关系图）**：提取两三个关键信息，分析其关系后下结论；注意材料中审判、行政等信息的关联，结合时代背景论述。
+## 复习重点
+- **小论文写作结构**：观点必须明确亮出，不能只是几个方面加名词的简单陈述；论证一般写两到三条，太少无法支撑论点、太多则冗长。
+- **论证罗列逻辑**：可按时间脉络（如先秦、明清时期）、国内外、内政外交等维度罗列，必须让阅卷者清楚看到所写条目，逻辑要清晰。
+- **结尾升华要求**：最后论述要简便并升华观点，不能简单把观点抄一遍；写结尾是为了升华观点，需注意与全文呼应。
+- **自命题类解题步骤**：先审题看要求（注意小红帽要求及形成标准），再读材料抓主要信息、细看关系，先写题目再罗列事实，控制时间后成文。
+- **观点提示类解题要点**：需选择核心观点并明确表述自己的判断（正确或错误），不能照抄材料；最后总结观点并进行升华。
+- **图表信息类解题方法**：迅速看题头、横向纵向信息，注意信息之间的关系变化，提取有效信息后再分析论述。
+## 学习建议
+- **审题放慢**：老师强调审题要慢，看清要求（如用世界史知识、限定范围），注意小红帽要求及形成标准，避免答偏。
+- **先打草稿再誊写**：题目先写好，罗列事实想清楚再写，不要直接写在答题卡上，避免写错又乱。
+- **结合时代背景分析**：写历史小论文要思考为何在该时期写此内容（如1940年抗战时期文人写作的目的），不能只罗列史实。
+- **多角度联想史实**：论证时结合政治、科技、文化等多方面史实（如丝绸之路、四大发明对欧洲影响），支撑观点更充分。</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>12357/2720</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="13.5" customHeight="1" s="9">
       <c r="A33" s="6" t="inlineStr">
@@ -11618,6 +12124,150 @@
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>政府报告</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t># 报告概况
+十四届全国人大三次会议于2025年开幕，由全国人大常委会主持，出席代表2880人，符合法定人数。会议第一项议程为审议政府工作报告，国务院总理李强代表国务院作报告。报告回顾2024年工作，提出2025年经济社会发展总体要求、主要预期目标及政府工作任务，整体基调为稳中求进、迎难而上，强调高质量完成“十四五”规划目标任务。2024年国内生产总值达134.9万亿元，增长5%；2025年主要预期目标为国内生产总值增长5%左右，城镇新增就业1200万人以上。
+# 核心政策
+## 2025年经济社会发展总体要求与政策取向
+- **总体要求**：坚持稳中求进工作总基调，完整准确全面贯彻新发展理念，加快构建新发展格局，扎实推动高质量发展，进一步全面深化改革，扩大高水平对外开放，建设现代化产业体系，更好统筹发展和安全，实施更加积极有为的宏观政策，推动经济持续回升向好，高质量完成`十四五规划`目标任务。
+- **政策基调**：充实完善政策工具箱，根据形势变化动态调整政策，提高宏观调控的前瞻性、针对性、有效性；强化宏观政策民生导向，经济政策的着力点更多转向惠民生、促消费，推动更多资金资源投资于人、服务于民生。
+## 2025年主要发展预期目标
+- **经济增长**：国内生产总值增长**5%左右**。
+- **就业**：城镇调查失业率**5.5%左右**，城镇新增就业**1200万人以上**。
+- **物价**：居民消费价格涨幅**2%左右**。
+- **收入与收支**：居民收入增长和经济增长同步，国际收支保持基本平衡。
+- **粮食安全**：粮食产量**1.4万亿斤左右**。
+- **能耗与生态**：单位国内生产总值能耗降低**3%左右**，生态环境质量持续改善。
+## 财政政策
+- **赤字安排**：今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**。
+- **超长期特别国债**：拟发行超长期特别国债**1.3万亿元**。
+- **特别国债**：拟发行特别国债**5000亿元**，支持国有大型商业银行补充资本。
+- **地方政府专项债券**：安排地方政府专项债券**4.4万亿元**。
+- **债务总规模**：今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**。
+- **支出结构**：加快各项资金下达，中央财政加大地方一般性转移支付力度，筑牢兜实基层`三保`底线；政府坚持过紧日子，腾出更多资金用于发展所需、民生所需。
+## 货币政策
+- **总体取向**：实施**适度宽松的货币政策**，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配。
+- **工具运用**：优化和创新结构性货币政策工具，更大力度促进楼市股市健康发展；进一步疏通货币政策传导渠道，推动社会综合融资成本下降。
+## 2025年政府工作十大任务
+### 一、大力提振消费、提高投资效益，全方位扩大国内需求
+- **提振消费专项行动**：实施`提振消费专项行动`，制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力，多渠道促进居民增收。
+- **消费品以旧换新**：安排超长期特别国债**3000亿元**支持消费品以旧换新。
+- **扩大服务消费**：扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力，强化消费者权益保护。
+- **扩大有效投资**：发挥好各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目、管好用好资金，坚决防止低效无效投资。
+- **投资规模**：今年中央预算内投资已安排**7350亿元**；用好超长期特别国债更大力度支持`两重`建设。
+- **民间投资**：优化地方政府专项债券管理机制，支持和鼓励民间投资发展，让民间资本有更大发展空间。
+### 二、因地制宜发展新质生产力，加快建设现代化产业体系
+- **培育新兴产业和未来产业**：深入推进战略性新兴产业融合集群发展，开展`新技术、新产品、新场景大规模应用示范行动`，培育生物制造、量子科技、具身智能、6G等未来产业。
+- **产业统筹布局**：加强产业统筹布局和产能监测预警，梯度培育创新型企业。
+- **传统产业改造升级**：深入实施`制造业重大技术改造升级和大规模设备更新工程`，加快制造业数字化转型，开展`标准提升引领传统产业优化升级行动`，打造名品精品经典产业。
+- **数字经济**：持续推进`人工智能+`行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展。
+### 三、深入实施科教兴国战略，提升国家创新体系整体效能
+- **高质量教育体系**：制定实施`教育强国建设三年行动计划`，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育，扎实推进优质本科扩容，加快`双一流`建设。
+- **教师队伍建设**：建设高素质专业化教师队伍，加强师德师风建设。
+- **科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革，加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目。
+- **科技成果转化**：健全科技成果转化支持政策和市场服务，加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境。
+- **人才队伍建设**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革。
+### 四、推动标志性改革举措加快落地，激发各类经营主体活力
+- **国有企业改革**：高质量完成`国有企业改革深化提升行动`。
+- **民营经济**：扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展`规范涉企执法专项行动`，政府寓管理于服务之中。
+- **全国统一大市场**：纵深推进全国统一大市场建设，破除地方保护和市场分割，综合整治`内卷式竞争`，修订出台新版市场准入负面清单，优化新业态新领域市场准入环境，构建统一的信用修复制度，完善企业简易注销制度。
+- **财税金融改革**：开展中央部门`零基预算改革试点`，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方；深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设。
+### 五、扩大高水平对外开放，积极稳外贸、稳外资
+- **稳定对外贸易**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设，拓展境外经贸合作区功能，支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点。
+- **吸引外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，加强外资企业服务保障，推动自贸试验区提质增效和扩大改革任务授权，持续营造市场化、法治化、国际化一流营商环境。
+- **共建一带一路**：推动高质量共建`一带一路`走深走实，统筹推进重大标志性工程和`小而美`民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局。
+- **多双边和区域经济合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制。
+### 六、有效防范化解重点领域风险，牢牢守住不发生系统性风险底线
+- **房地产市场**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子。
+- **地方政府债务**：完善和落实`一揽子化债方案`，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，完善政府债务管理机制，坚决遏制违规举债行为。
+- **金融领域风险**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险；健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案。
+### 七、着力抓好三农工作，深入推进乡村全面振兴
+- **粮食稳产保供**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`，加快先进适用农机装备研发应用和农业科技成果大面积推广。
+- **巩固脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫，加强易地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系。
+- **农村改革**：有序推进第二轮土地承包到期后再延长**30年**试点，扩大整省试点范围。
+- **乡村建设**：因地制宜推动兴业强县富民一体发展，拓宽农民增收渠道，持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村。
+### 八、推进新型城镇化和区域协调发展，优化发展空间格局
+- **新型城镇化**：深入实施`新型城镇化战略行动`，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务，强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道。
+- **城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市。
+- **区域战略**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极，支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东中西东北地区产业协作。
+### 九、协同推进降碳、减污、扩绿、增长，加快经济社会发展全面绿色转型
+- **污染防治和生态建设**：持续深入推进`蓝天碧水净土保卫战`，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程，积极推进`美丽中国先行区`建设。
+- **绿色低碳经济**：深入实施`绿色低碳先进技术示范工程`，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用，健全绿色消费激励机制。
+- **碳达峰碳中和**：积极稳妥推进碳达峰碳中和，建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度，加快建设`沙戈荒`新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理。
+### 十、加大保障和改善民生力度，提升社会治理效能
+- **稳定和扩大就业**：实施`重点领域、重点行业、城乡基层和中小微企业就业支持计划`，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障，开展大规模职业技能提升培训行动。
+- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施`医疗卫生强基工程`，优化药品集采政策，强化质量评估和监管，健全药品价格形成机制，支持创新药发展，完善中医药传承创新发展机制，加强疾病预防控制体系建设，严格医保基金监管。
+- **社会保障和服务**：城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金，推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、康复辅助器具购置和租赁支持力度；制定促进生育政策，发放育儿补贴，大力发展托幼一体服务；完善分层分类社会救助体系。
+- **精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业，推动优质文化资源直达基层，健全文化产业体系和市场体系，推进群众身边的运动场地设施建设，广泛开展全民健身活动，加强青少年科学健身和健康干预。
+- **国家安全和社会稳定**：全面贯彻总体国家安全观，深入实施`安全生产治本攻坚三年行动`，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对，推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国。
+# 重点工作
+## 大力提振消费、提高投资效益，全方位扩大国内需求
+- **提振消费专项行动**：实施提振消费专项行动，制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力，多渠道促进居民增收。
+- **消费品以旧换新**：安排超长期特别国债3000亿元，支持消费品以旧换新。
+- **扩大服务消费**：扩大健康、养老、托幼、家政等多元化服务供给；加快数字、绿色、智能等新型消费发展；释放文化、旅游、体育等消费潜力。
+- **消费者权益保护**：强化消费者权益保护，营造安心放心消费环境。
+- **扩大有效投资**：发挥好各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目，管好用好资金，坚决防止低效无效投资。
+- **投资安排**：今年中央预算内投资已安排7350亿元；用超长期特别国债更大力度支持"两重"建设；优化地方政府专项债券管理机制。
+- **民间投资**：支持和鼓励民间投资发展，让民间资本有更大发展空间。
+## 因地制宜发展新质生产力，加快建设现代化产业体系
+- **培育新兴产业和未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动；培育生物制造、量子科技、具身智能、6G等未来产业。
+- **产业统筹布局**：加强产业统筹布局和产能监测预警，梯度培育创新型企业，让更多企业在新领域新赛道跑出加速度。
+- **传统产业改造升级**：深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型，开展标准提升引领传统产业优化升级行动，打造名品精品经典产业。
+- **数字经济创新**：持续推进"人工智能+"行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展。
+## 深入实施科教兴国战略，提升国家创新体系整体效能
+- **高质量教育体系建设**：制定实施教育强国建设三年行动计划，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育；扎实推进优质本科，加快"双一流"建设；建设高素质专业化教师队伍，加强师德师风建设。
+- **高水平科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革；加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目；健全科技成果转化支持政策和市场服务；加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境。
+- **人才队伍建设**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革，鼓励各类人才潜心钻研、厚积薄发。
+## 推动标志性改革举措加快落地，更好发挥经济体制改革牵引作用
+- **激发经营主体活力**：坚持和落实"两个毫不动摇"，高质量完成国有企业改革深化提升行动；扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动。
+- **服务企业**：政府要寓管理于服务之中，用服务的暖心增强企业的信心。
+- **全国统一大市场建设**：纵深推进全国统一大市场建设，破除地方保护和市场分割，综合整治"内卷式"竞争；修订出台新版市场准入负面清单，优化新业态新领域市场准入环境；构建统一的信用修复制度，完善企业简易注销，逐步推广新主体活动发生地统计。
+- **财税金融体制改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革；加快推进部分品目消费税征收环节后移并下划地方；深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设。
+## 扩大高水平对外开放，积极稳外贸、稳外资
+- **稳定对外贸易**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面；促进跨境电商发展，加强海外仓建设，拓展境外经贸合作区功能；支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点。
+- **吸引外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点；加强外资企业服务保障，推动自贸试验区提质增效和扩大改革任务授权；持续营造市场化、法治化、国际化一流营商环境。
+- **共建"一带一路"**：统筹推进重大标志性工程和"小而美"民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局。
+- **多双边和区域经济合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制，扩大同各国利益的汇合点，促进共同发展。
+## 有效防范化解重点领域风险，牢牢守住不发生系统性风险底线
+- **房地产市场**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险；加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子。
+- **地方政府债务**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，完善政府债务管理机制，坚决遏制违规举债行为。
+- **金融领域风险**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险；健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案，有效维护金融安全稳定。
+## 着力抓好"三农"工作，深入推进乡村全面振兴
+- **粮食稳产保供**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广。
+- **粮食安全责任**：各地区都要扛稳保障国家粮食安全责任，共同把饭碗端得更牢。
+- **巩固脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫；加强易地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度；统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系。
+- **农村改革发展**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围；因地制宜推动兴业、强县、富民一体发展，拓宽农民增收渠道；持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村。
+## 推进新型城镇化和区域协调发展，进一步优化发展空间格局
+- **新型城镇化**：深入实施新型城镇化战略行动，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务；强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道。
+- **城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市。
+- **区域战略实施**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极；支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东、中、西、东北地区产业协作。
+## 协同推进降碳、减污、扩绿、增长，加快经济社会发展全面绿色转型
+- **污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程，积极推进美丽中国先行区建设。
+- **绿色低碳经济**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用，健全绿色消费激励机制，推动形成绿色低碳生产方式和生活方式。
+- **碳达峰碳中和**：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度，加快建设"沙戈荒"新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理。
+## 加大保障和改善民生力度，提升社会治理效能
+- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换；优化就业创业服务，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障；开展大规模职业技能提升培训行动。
+- **就业导向**：让多劳者多得、技高者多得、创新者多得。
+- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程；优化药品集采政策，强化质量评估和监管；健全药品价格形成机制，支持创新药发展；完善中医药传承创新发展机制；加强疾病预防控制体系建设；严格医保基金监管，让每一分钱都用于增进人民健康福祉。
+- **社会保障和服务**：城乡居民基础养老金最低标准再提高20元，适当提高退休人员基本养老金；推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、辅助器具购置和租赁支持力度；制定促进生育政策，发放育儿补贴，大力发展托幼一体服务；完善分层分类社会救助体系，保障困难群众基本生活。
+- **精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业；推动优质文化资源直达基层，健全文化产业体系和市场体系；推进群众身边的运动场地设施建设，广泛开展全民健身活动；加强青少年科学健身和健康干预，让年轻一代在运动中强意志、健身心。
+- **国家安全和社会稳定**：全面贯彻总体国家安全观，加强公共安全治理，深入实施安全生产治本攻坚三年行动，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对；推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国。
+## 政府自身建设
+- **规划编制**：今年将开展"十五五"规划编制工作，科学确定发展目标，谋划好重大战略任务、重大政策举措、重大工程项目，更好发挥规划对经济社会发展的引领指导作用。
+- **法治政府建设**：严格依照宪法法律履职尽责，自觉接受同级人大及其常委会的监督，自觉接受人民政协的民主监督，自觉接受社会和舆论的监督，加强审计监督。
+- **行政效能提升**：善于把党中央决策部署和自身实际结合起来，提高创造性贯彻落实能力，切实把面向基层的督查检查考核减下来，让广大干部把更多时间和精力用到干实事上。
+- **廉政建设**：深入贯彻中央八项规定精神，坚定不移推进政府党风廉政建设和反腐败斗争，全面提升政府履职能力，确保党中央决策部署不折不扣落实到位。</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10273/9477</t>
         </is>
       </c>
     </row>
@@ -11827,6 +12477,72 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t># 全文摘要
+景城苑小区召开物业招标答疑与评标会，业主委员会代表与两家物业公司（长沙富佳物业、深圳市资平物业）参与，围绕小区改造计划、承接查验、安防停车管理、包干制经验、楼层杂物处理等议题进行问答。富佳物业提出一年内完成改造，针对车辆乱停先分析原因再增加停车位或派保安客服现场劝阻；承接查验提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先私下沟通，再请业委会或街道社区协调，必要时在许可下采取强制措施。资平物业介绍公司成立于2004年，总部在深圳，全国367个项目、127个业委会项目，创始人陈志平为万科物业创始人，为中国物业管理协会副会长单位、全国百强企业；景城苑项目人员配置16人，一线人员不外包，进场第一个月集中整改环境绿化，半年内完成设备设施排查，八个月内保证项目有效运作。评标委员会打分后，长沙富佳物业72.91分、湖南恒居恒基居业物业60.73分、重庆新东源物业54.48分，最终确定深圳市资平物业发展有限公司为中标候选人；打分环节全程保密，暂停网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。
+# 分段速览
+## 00:00:10–00:10:00 富佳物业答疑
+业主代表就改造计划、停车管理、承接查验、安防停车、满意度与收费率等提问，发言人1逐一回答。富佳物业提出预计改造时间一年内完成；针对车辆乱停先分析原因，若停车位不够则增加停车位，若业主不自觉则派保安客服现场说服劝阻；承接查验提前两周项目负责人入场摸底、提前一周服务人员到位培训；交接不畅时先与现物业私下沟通，无法解决则请业委会或街道社区协调，必要时在许可下采取强制措施；安防改善措施包括增设人行门禁系统、升级大堂报到系统、增设隔离墩、建设外围停车场并安装停车管理系统、增设电动车停车场；处理业主问题采用四句话：用心倾听、如实记录、马上处理、及时反馈。
+## 00:10:00–00:19:44 资平物业公司介绍
+资平物业代表介绍公司背景：成立于2004年，总部在深圳，全国367个项目，127个业委会项目，创始人陈志平为万科物业创始人，协同建立中国第一个业委会，为中国物业管理协会副会长单位、全国百强企业。景城苑项目人员配置16人，薪酬福利高于周边同类项目，一线人员不外包。进场第一个月调动湖南战队资源进行环境绿化清洁整改，半年内完成设备设施排查，八个月内保证项目有效运作。导入顾客管理系统，集中处理业主投诉咨询，形成大数据指导工作。长沙有11个项目，其中10个包干制，1个酬金制。
+## 00:19:44–00:34:44 资平物业答疑
+业主代表就改造时间、包干制经验、承接查验、安防停车、楼层杂物处理等提问，资平物业代表逐一回答。改造计划为第一个月环境绿化、半年内设备设施、八个月集中整改，一年内达到有序状态；包干制方面强调财务透明、保障业主知情权，团队30%为现有干部、60%左右为现有物业优秀员工及新招聘；承接查验时增派150%人员，分专业组验收，调动集团工程师协助；停车管理方案包括收集业主车辆信息、升级道闸、制定停车公约；楼层杂物处理以疏导为主，设置临时堆放区、集中晾晒区，提供免费上门晾晒服务。
+## 00:34:44–00:35:33 评标与结果公布
+评标委员会打分后，主持人公布各公司得分：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源物业管理有限公司54.48分。评标确定深圳市资平物业发展有限公司为中标候选人。打分环节全程保密，暂停网络直播，录像材料不予公开；总评委打分去掉一个最高分和最低分。
+# 要点梳理
+## 富佳物业答疑
+- **改造计划**：富佳物业预计在一年内完成全部改造项目，具体12大改造点详见标书第117页。
+- **车辆乱停应对**：先分析乱停原因（停车位不够、停车位置太远或业主不自觉），停车位不够则增加停车位，业主不自觉则派保安、客服人员现场说服、劝阻、纠正。
+- **承接查验安排**：提前两周项目负责人入场摸底小区现场情况；提前一周服务人员全部到位并培训公司制度与操作流程。
+- **交接不畅应对**：先与现物业私下沟通了解诉求，公司间能解决则直接解决；不能解决则请业委会或街道社区组织现场协调会；仍无法解决时，在业委会、业主大会及街道社区许可下采取强制措施。
+- **安防改善措施**：大门口增设人行门禁系统（支持手机微信、刷卡、密码进出）；升级大堂报到系统，录入业主车辆信息统一管理，临时车辆由安保登记放行并询问；地面增设隔离墩，禁止公共场所停车，保障消防通道与人行通道畅通；建设外围停车场并安装停车管理系统；增设电动车停车场（考察发现电动车乱停与停车位不足有严重关系）。
+- **业主问题处理原则**：四句话——用心倾听、如实记录、马上处理、及时反馈；处理完成后及时向业主反馈完成时间，业主可联系确认。
+## 资平物业公司介绍
+- **公司背景**：资平物业成立于2004年，总部在深圳，为全市场化物业公司（无开发背景），全国367个项目，其中127个为业委会项目。
+- **创始人渊源**：公司创始人陈志平原为万科物业创始人，在深圳从事物业管理时协同建立中国第一个业委会。
+- **行业资质**：为中国物业管理协会副会长单位、全国百强企业，业务涉及社会公司和循环养老。
+- **管理理念**：打造「让一线权利归还业主」，所有业委会项目财务透明（包干制每季度公示物业管理费、停车费等财务），管理透明（招标、外包等事项让业主代表参与）。
+- **团队配置**：景城苑项目人员配置16人，薪酬福利保证高于周边同类项目，一线人员全部直招不外包（长沙项目有外包影响服务品质的经验教训）。
+## 资平物业改造计划
+- **四步举措**：第一步「洗理静音」——进场第一个月调动湖南战队其他项目人员资源，对小区环境、绿化、清洁、杂物进行全面清扫，保证感官上干净整洁有序。
+- **设备设施整改**：第二步「疏金活选」——调动集团设备公司水电、给排水、电梯、消防工程师，对小区所有设备设施全面排查诊断，在投资范围内集中改造。
+- **疑难问题处理**：第三步「疑难杂症」——涉及消防、渗水等重大问题，全面检查后提供意见，经业委会授权或召开业主大会进行招投标。
+- **品质提升**：第四步「有效提升」——将总部管理标准、前沿管理经验及与业主、业委会沟通经验延续到项目。
+- **时间规划**：进场第一个月完成环境绿化整改，半年内完成设备设施排查，八个月以内保证项目有效运作，一年内保证小区达到有序状态。
+- **顾客管理系统**：全面导入顾客管理系统，集中处理业主投诉、咨询、报事，保证有人跟进、有人回访；根据每月投诉报事数据形成大数据，指导下月工作重点（如10月业主对门岗管控有意见，11月重点改善）。
+- **社区活动**：根据小区老龄情况开展适老活动（如教老年人发抖音、服装帽林打造），按小区不同团体（跳舞、打篮球）开展社区文化活动，公司硬性标准为每两个月开展一次。
+## 资平物业答疑
+- **改造着手方向**：经查勘，景城苑主要存在四方面问题——安全管控、设备设施管理与维护、环境、社区氛围打造。
+- **改造具体措施**：进场一个月集中资源整改环境绿化、楼道杂物、牛皮癣等感官较差处；利用集团工程师排查设备设施，投资款内快速整改，需动用维修资金的与业主沟通或启动业主大会授权；针对业委会和业主关注的问题进行优先整改。
+- **包干制经验**：长沙11个项目中10个为包干制、1个为酬金制；包干制下保证财务透明、业主知情权，增加与业委会和业主的互动，让业主参与物业管理。
+- **团队组建**：管理干部30%从集团现有人员选拔，60%左右吸收现有物业优秀员工或重新招聘，保证团队整体优秀。
+- **公益性服务**：长沙项目居家上门服务员工免费、材料费由业主自买或物业代购；开展家政、24小时业主护送服务等有偿和无偿业务。
+- **承接查验准备**：前期与社区街道、派出所沟通，与现物业和业委会明确设备设施、债务债权等事项；按专业线分专业组验收，调动集团工程师协助查出问题，避免遗留不明问题。
+- **承接查验人员增派**：在现有16人团队基础上增派150%人员，有成熟的承接查验和数字化小组。
+- **停车管理方案**：收集小区业主车辆信息，制定整体停车管理方案（含禁区停放），升级道闸识别外来人员与业主亲戚来访，形成停车管理制度和公约。
+- **监控技术手段**：通过自有设备公司和平台，在技术层面解决关键岗位和关键部位监控问题。
+- **楼层杂物处理**：以宣传引导为主，通过上门宣传、海报、法律知识宣传让业主认识堆放杂物的风险与法律责任；与社区、应急管理部门联合行动；提前沟通并给业主处理杂物的时间段；可设置临时堆放区供业主短期存放，限期解决。
+- **晾晒问题处理**：湖南阴雨天气多，业主有晾晒需求，可在小区寻找位置设置集中晾晒区；有项目提供免费增值服务——太阳大时物业工作人员上门取被子晾晒，早上拉出、晚上送回。
+## 结论与决定
+- **评标结果**：深圳市资平物业发展有限公司为中标候选人，得分排名第一。
+- **各公司得分**：长沙富佳物业管理有限公司72.91分，湖南恒居恒基居业物业管理有限公司60.73分，重庆新东源物业管理有限公司54.48分。
+- **打分规则**：总评委打分去掉一个最高分和最低分；打分环节全程保密，暂停会场网络直播，录像材料不予公开；除评委、监督员及必要会务人员外，其余人员退场。
+- **评标程序**：抢标时间10分钟，每道答题时间3分钟。
+## 待确认与风险
+- **小区现状问题**：车辆停放不规范、电动车乱停；监控门禁失效导致人员车辆随意进出；小区停车管理混乱。
+- **楼层安全隐患**：楼层顶层存在堆放杂物或乱搭乱晒问题，需在不激发矛盾前提下解决。
+- **交接风险**：与原物业交接可能出现不畅，需提前准备应对措施。</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11743/4102</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="13.5" customHeight="1" s="9">
       <c r="A35" s="6" t="inlineStr">
@@ -11942,6 +12658,69 @@
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本期视频由主讲人李正讲述康熙朝文渊阁大学士陈廷敬的一生，以“妈妈张氏的开蒙”“圣祖康熙的讲师”“至公无私的落幕”三个阶段为骨架，旨在澄清影视剧与史实的差异，并回答“陈廷敬凭什么让康熙念念不忘”这一核心问题。陈廷敬本名陈敬，字子端，号午亭，1638年出生于山西泽州府阳城县，21岁中进士并入翰林院，因与直隶庶吉士陈敬同名，22岁主动上书顺治请求改名，顺治赐名“廷敬”。讲座的核心主张在于：陈廷敬虽无平三藩、收台湾、剿灭噶尔丹等显赫功绩，却以一生清廉正直、恪守初心赢得康熙的持久信任，临终前康熙仍询问“大臣中学问人品如大学士可代理内廷事务者为谁”。关键锚点包括：陈廷敬6岁前由母亲张氏口授背诵《论语》《孟子》《大学》《中庸》《诗经》；14岁以全省第一考中秀才；康熙42年66岁时升任文渊阁大学士并总理南书房事务；康熙49年73岁第四次申请退休获准，康熙赐匾额“午亭山村”及楹联“春归乔木浓阴茂，秋到黄花晚节香”。讲座面向对清代名臣生平与康熙朝政治感兴趣的观众，通过陈廷敬从母亲开蒙到位极人臣的完整履历，展现“苟正其身矣，于从政乎何有”的为官之道，对理解清代官僚体系与君臣关系具有参考意义。
+# 核心观点与论证
+## 母亲张氏开蒙奠定根基
+- **开蒙方式**：陈廷敬6岁外出上学前，母亲张氏口授其背诵《论语》《孟子》《大学》《中庸》《诗经》，史载“凡四子书毛诗皆太夫人口授以诵”。
+- **母亲背景**：张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，嫁入陈家后“家政稍暇即出书籍”，常读书至半夜，比科举书生更用功。
+- **鼓励教育**：陈廷敬9岁作诗《咏牡丹》，其中“要使误接春”一句获母亲夸赞“我儿子这就是天才”，童年学习大半在母亲关照下完成。
+- **科举成绩**：顺治八年（1651年）14岁以全省第一考中秀才，20岁中举人，21岁中进士并入翰林院任庶吉士；顺治18年（1661年）24岁庶吉士毕业考试考取同届第一，获授秘书院检讨。
+## 改名风波与顺治赏识
+- **同名冲突**：陈廷敬入翰林时本名陈敬，与直隶通州庶吉士陈敬同名；顺治因直隶陈敬满文考试不及格点名批评并罚俸一年，未带籍贯导致翰林院风言风语波及两人。
+- **主动改名**：22岁陈廷敬主动上书顺治请求改名，史载“庶吉士陈敬奏请更名廷敬，以与直隶庶吉士陈敬同名故也”。
+- **御赐名字**：据李光地记载，陈廷敬的“廷”字系顺治所赐，改名后既与直隶陈敬撇清关系，又借御赐之名与顺治拉近关系；顺治与陈廷敬同为崇祯11年出生，同年同岁且欣赏其才华。
+## 康熙讲师与教学风格
+- **仕途升迁**：康熙六年（1667年）陈廷敬考察一等称职，两年后32岁升任正六品国子监司业；康熙11年（1672年）35岁充日讲起居注官，康熙15年（1676年）39岁充经筵讲官。
+- **整顿国子监**：陈廷敬任国子监司业时废除学生拜见须送见面礼的不成文规定，史载“凡诸生以至献者悉屏去之”，学生越送礼越不见，不送礼才愿见。
+- **教学风格**：讲评经史“特别狠辣，对就骂错就骂，从不含糊其辞”，曾指史书痛骂孙权背刺关羽“孙权简直就是猪是狗”，康熙欣赏其坚定三观与外放风格。
+- **执掌翰林院**：康熙16年（1677年）正月，陈廷敬出任翰林院掌院学士，教习当届庶吉士。
+## 母亲丧礼破满汉之别
+- **康熙表态**：康熙16年母亲张氏病逝，终年59岁；康熙召集大臣称“满汉大臣俱系一体，汉大臣有丧，亦应遣大臣往祭”，派大学士明珠、掌院学士喇沙里携茶酒往祭。
+- **礼部反对**：礼部以陈廷敬母亲封号系詹事府詹事时授予、按例三品不得祭奠为由反对，康熙回应“以平靖世将握秦而恩福待，吾何以劝劳臣乎”，强调好大臣必须给予高尊重。
+- **破格祭奠**：康熙下令即刻追封陈廷敬母亲，按学士品级由官方派人祭奠，张氏以女儿身读书教子，临终丧事获中央派官带天子吊孝。
+## 左都御史整顿吏治
+- **捐纳考试**：康熙23年（1684年）47岁陈廷敬升任从一品左都御史，上奏捐纳买官者正式上岗前须追加考试，“文艺略小者给予录用，否则且令异业听其再试”。
+- **康熙支持**：吏部以“以前补用人员从未考试”反对，康熙支持陈廷敬并补充令各地督抚详查已任命官员，“凡临民之官内有不识字义者，着该督抚不时实行查参修治”。
+- **全面弹劾**：针对各省督抚作风问题、地方政府赈灾懒政问题严查弹劾，一边指出问题一边给出解决方案，亲自拟定新的赈灾报批流程。
+- **三部尚书**：随后两年连续出任工部、户部、吏部三部尚书，“人到哪里就整顿到哪里”，面对劝其“和光同尘”的劝告，表示“只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，也是无所谓的”。
+## 张谦案牵连与清白复出
+- **案件经过**：康熙26年（1687年）50岁，湖广巡抚张谦因贪污被抓，供称曾贿赂陈廷敬、徐乾学、高士奇，并拿出三人劝其好好当官的信件作为索贿证据。
+- **自辩与处理**：陈廷敬自辩“从来没有跟他有过什么特殊往来”，称张谦因自己过于疏远而怨恨攀咬；康熙传旨主审官马齐“只处理张谦一个人，不得扩大株连”，其他人等事后密查。
+- **辞官复出**：51岁陈廷敬主动上书辞官，康熙准许其辞官但留京修书；康熙29年（1690年）53岁辞官一年后复出，再次出任左都御史，康熙以此宣告其清白。
+- **清白佐证**：主讲人给出三点理由：据李光地记载张谦案系徐乾学一手策划；徐乾学贪污事迹多且热衷结党；同案徐乾学、高士奇后来均因贪污被罢官，唯独陈廷敬复出任全国最高监察长官。
+## 位极人臣与晚年荣退
+- **大学士任上**：康熙42年（1703年）66岁升任文渊阁大学士，总理南书房事务，是内阁中唯一既管南书房又任经筵讲师的大学士；康熙以“机务重地，良难其人”拒绝其退休请求。
+- **四次请退**：70岁、71岁、72岁连续三年三次申请退休均被拒，康熙49年（1710年）73岁第四次申请终获准。
+- **御赐匾联**：康熙亲赐匾额“午亭山村”和楹联“春归乔木浓阴茂，秋到黄花晚节香”，并称“朕特殊匾联赐卿，自此不与人写字矣”。
+- **身后哀荣**：两年后陈廷敬病逝，终年75岁，谥号文贞；康熙包办治丧费用，从大内找紫砂碗做棺材，令皇三子允祉及大臣侍卫往祭，命各部院满汉大臣往吊。
+# 金句总结
+&gt; “朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？”
+- 背景：康熙在陈廷敬临终前询问，还有谁可代理内廷事务，足见对其人品学问的倚重。
+&gt; “要使误接春，定须春恨事。”
+- 背景：陈廷敬9岁作《咏牡丹》，母亲张氏听后夸其为天才。
+&gt; “自古未有不晓文艺之人可以为民父母者也。”
+- 背景：陈廷敬任左都御史时上奏，主张捐纳买官者上岗前必须追加考试，不识字义者不得为官。
+&gt; “我贤与虽折且怨，庸和尚说。”
+- 背景：有人劝陈廷敬官场应和光同尘，他回应只要人正事对，受点挫折埋怨也无所谓。
+&gt; “苟正其身矣，于从政乎何有？”
+- 背景：主讲人引《论语》总结陈廷敬一生——自身品行端正，治理政事便无困难。
+&gt; “春归乔木浓阴茂，秋到黄花晚节香。”
+- 背景：康熙赐陈廷敬楹联，赞其一生干净、晚节不亏。
+# Q&amp;A 环节
+未提及</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>9132/3019</t>
         </is>
       </c>
     </row>
@@ -12559,6 +13338,63 @@
           <t>采访记录</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t># 访谈概述
+本期《锵锵三人行》由主持人窦文涛与嘉宾马未都、《明朝那些事儿》作者当年明月（石悦）围绕刚播完的日剧《大奥》展开对日本文化的讨论，随后转入明朝历史话题，探讨明史写作缘由、朱元璋评价、明朝兴亡经验与明式家具地位等。受访者身份照原文：当年明月为《明朝那些事儿》作者，马未都为家具收藏家。访谈主线覆盖《大奥》与日本文化、明朝历史与明史写作、明朝皇帝与明式家具三块议题。受访者核心观点：日本文化强调极端精神，做事做到尽头，是忠诚文化的典型国家，战后用30年成为世界第二经济强国（绝对量而非人均量），是唯一没有资源的强国；中国中庸、日本极端，日本文化中忠诚与集体规则意识强，聪明人没有生存环境；历史教训是“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”。原文锚点：日剧《大奥》三部曲、明朝260多年、1644年明朝灭亡。看点：当年明月指出正德皇帝被嘉靖时期编写的实录抹黑，从江南回来在通州停半年、先派人打探京城情况，显示其有城府；马未都提出故宫大红大紫是满族趣味，宋明汉人文人政权审美素雅。
+# 访谈详细记录
+## 日剧《大奥》与日本文化
+- **《大奥》历史背景**：嘉宾指出该剧分三部，前两部对应中国晚清到清初时段，第三部在明治维新之前，是一部有跨越性的历史剧。
+- **大奥释义**：嘉宾解释“大奥”即普通话所说的后宫，日本话中“奥”指很深的地方，如“深奥”一词即保留此意；大奥规矩严谨，后宫不许进人。
+- **日本极端精神**：受访者认为《大奥》体现日本文化从头到尾未变的“极端精神”，即所有事情要做到尽头；战后日本用30年成为世界第二经济强国（绝对量而非人均量），是唯一没有资源的强国，这不是偶然而是必然。
+- **中日文化对比**：受访者认为中国文化精神是中庸，讲究在正确与错误之间找一条最适合的路；日本精神恰恰相反，坚持一个原则做到极致，如炮手忘记一切只记得把炮开出去即达最高境界。
+- **忠诚文化**：受访者认为日本是忠诚文化的典型国家，强调忠诚与守本分；以剧中阿福为例，25岁进大奥当奶妈，65岁去世，40年做事不处私心、完全公心，被伤害的对方都认为她出于公心。
+- **日本社会实例**：受访者讲述参观日本豆腐厂经历，豆腐规定当天做当天卖，夜里11:45所有人坐等，12点整准时开工，4点多干完上市；又举做绳子者为例，几年内不赚钱铺市场，最终以4%差价获利。
+- **日本人生存观**：受访者认为日本没有资源、常发火山地震，人对世界有极强求生欲望且偏悲观，必须融入团体按固定规则做事才能生存；日本聪明人没有生存环境，社会文化抵制非常难过。
+- **对死亡的态度**：受访者认为日本人看樱花只看落的那一天，对死亡不是藐视而是有点向往或不惧怕，这与岛国生态环境恶劣有关；另一嘉宾则认为日本民族不是藐视生命而是重视，经济危机时很多身家万贯者选择自杀。
+## 明朝历史与明史写作
+- **写明史缘由**：受访者（《明朝那些事儿》作者）表示写明史是因为明史资料最多、他最熟；历史研究有两个难点，一是先秦（史料少、多靠编），二是明清（一个事件可能有七个不同说法，如同罗生门）。
+- **推崇朱元璋**：受访者认为朱元璋是历史上由最底层（乞丐）坐上皇位的人，刘邦好歹算村长；他因知道每一层猫腻而疑心重，从一起干到推翻元朝、当上皇帝，明朝规章制度由他定下且基本无大改动。
+- **英雄史观**：受访者认为人的因素最大，改变时势一定是出现一个人；以朱元璋为例，他天分相当高，如同《亮剑》中的李云龙，没上过军事院校但能打仗，靠的是战场上积累的经验。
+- **朱元璋起义的偶然性**：受访者讲述朱元璋原在庙里犹豫是否参加起义军，因信差送信被人听到告发，没办法才去起义；他强调历史最重要的是明白“这事是真的”，旁观者觉得好玩，但当事人是冒着掉脑袋的风险。
+- **明朝兴亡经验**：受访者认为明朝经验有体现，如仁宣盛世、晚明老百姓生活很好；明末江南市民生活特别轻松，想去哪去哪，江浙工商业兴起，出现三言二拍等娱乐产品，说明有养活自己的资本。
+- **明末艺术与生活**：受访者指出明末工艺品变得非常精细，日本派大量工匠来交流学习；吴门画派如文征明、唐寅生活安逸，画的是小桥流水、风雨归舟图，充满欣赏感；到八大山人时画翻白眼，是因对社会愤愤不平。
+- **历史教训**：受访者引用名言“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，认为历史事件发生时有背景，不能套用经验；史书记载如同照片，而古人的生活是录像，不知道那一幕之前和之后是什么。
+- **明朝灭亡原因**：受访者提到1644年明朝灭亡时北京发生瘟疫“疙瘩瘟”，可能是天花；他与老师交流认为明朝亡得蹊跷，什么坏事都赶上了。
+- **王朝三百年大限**：嘉宾指出中国历史王朝300年是大限，逼近300年自己就没了，如同人到八九十岁大限将至；严格讲超过300年的只有宋朝（南北宋接上，退让大半个国土延续），汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
+## 明朝皇帝与明式家具
+- **正德皇帝被抹黑**：受访者认为正德皇帝被评价为荒淫，但可能被嘉靖时期编写的《明武宗实录》抹黑——因嘉靖是堂兄弟接班，不能把前任写得太好；正德皇帝从江南回来在通州停半年，先派人打探京城有无埋伏，显示很有城府。
+- **正德皇帝与豹房**：受访者指出豹房其实是动物园，养了豹子，后宫也是女人，放哪都一样；另一嘉宾补充正德皇帝没少找女人但不留种，没有正宗传下来，到嘉靖是拐弯。
+- **天启皇帝当木匠**：嘉宾讲述天启皇帝爱当木匠，干完活拆了卖，卖完还打听卖得怎么样，成就感特大；这从侧面反映当时社会对家具的重视，明式家具在国际上地位高绝非偶然。
+- **明式家具地位**：嘉宾认为所有偶然中一定有必然因素，皇帝能下那么大力气做家具，可见家具在每个人心里地位高；宋明是典型汉人文人政权，文人审美较高，对美的判断不是表象的，而满族对美的判断是表象的，故宫大红大紫是满族趣味。
+- **明朝皇帝个性**：受访者指出明代皇帝确实没什么事干，明神宗几十年不上朝但不出去；明朝皇帝被后人说差，是因为接班的嘉靖不是正德儿子而是堂兄弟，拐了个弯，所以不能把他写得太好。
+# 关键引语与金句
+&gt; “慢慢来才是最快的方法。”
+- 背景：谈到日本文化中做事不夹杂私心、按各自本分行事时，受访者引述他人之语说明“不偷奸耍滑”反而是更有效的成功路径。
+&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
+- 背景：回应主持人关于明朝兴亡经验教训能否借鉴的提问，受访者以此概括历史经验难以直接套用的观点。
+&gt; “你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办。”
+- 背景：解释为何历史教训难以吸取——后人常自以为聪明，但历史事件发生时有其特定背景，身处其中未必能做得更好。
+&gt; “史书上记载下来的是照片，而我们实际上古人的生活都是录像。”
+- 背景：受访者用照片与录像的比喻，说明史书只留下瞬间定格，后人看不到事件的前因后果，因此容易对历史产生误解。
+&gt; “日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是中庸。”
+- 背景：对比中日文化差异时，受访者以中庸概括中国文化精神，与日本文化的极端精神相对照。
+&gt; “他是完全每个人发自内心的……他全民族的这种极端精神，是一个国家在战后这样一个不利的局面下，只需要30年的时间，他进入世界第二经济强国。”
+- 背景：谈到日本战后30年成为世界第二经济强国（绝对量而非人均量）时，受访者将其归因于全民族的极端精神。
+&gt; “明史我最熟，为什么我最熟呢？因为明史的资料最多。”
+- 背景：回应主持人及记者关于“为什么写明史”的提问，受访者给出最直接的原因。
+&gt; “一个说法可能有七个不同，一个事件可能有七个不同的说法，就好像那个罗生门。”
+- 背景：解释明清史研究之难——史料虽多但说法纷杂，同一事件存在多种相互矛盾的记载。</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17496/3309</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="13.5" customHeight="1" s="9">
       <c r="A37" s="6" t="inlineStr">
@@ -12924,6 +13760,67 @@
           <t>采访记录</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t># 访谈概述
+余华在访谈中回顾其写作生涯，将文学创作分为1.0、2.0、3.0三个阶段：1.0阶段强调逼自己坐下来写，让屁股和椅子建立友谊；2.0阶段受卡夫卡启发，写作越写越难，遇到心理表现障碍；3.0阶段受威廉·福克纳影响，采用视觉描写，让心脏停止跳动，让眼睛睁开。他认为3.0版本已经足够，已经是大海，此后未再升级。余华谈到《兄弟》创作始于1996年，因中国社会变化复杂而写，2004年重新写时庆幸96年没写完，因为2004年的变化更大。他认为最好的写作状态在40多岁到50岁，但那段时光被浪费，只出了两部作品。他2006年开始写一部长篇小说，实践跨度与《兄弟》相同，从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写，但感觉已远去。他估计自己能够好好写作的时间可能还有十年左右。余华回忆《兄弟》出版时期待一片赞扬，结果一片骂声，他努力解释但效果不佳；《第七天》出版时只接受一个采访，让朋友做好挨骂准备，结果果然一片骂声；《文城》骂声少一些。他总结对待批评的方式：第一不要看，第二有些批评要重视。他认为批评宋凡平太完美没有道理，因为宋凡平是阶段性人物；而《第七天》有批评说社会底层人未必都善良，这句话说得很好，会在以后写小人物时考虑进去。余华谈到互联网上关于他的话有一半不是他说的，曾停了一年活动进入冷静期，但自媒体时代会把几十年前的事情翻出来。他面对中年危机，认为只有写作能得到新的东西。他的自我调节方法是选择让自己知道什么，不知道什么，屏蔽负面消息。他不担心热度消散，因为他的工作是写作，不是说话。余华谈到不再追求高度，追求宽度，认为这一代作家被马尔克斯误导，想在一本书里写一个世纪的故事，但没有能力在不到30万字的小说里写出一个世界。他计划先写完一个喜剧，改变读者对他的印象。他希望下一步作品在2029年之前完成，计划开学时与学生见面，处理学校事务后回三亚继续写作。余华分享童年第一次看到大海的感受，认为人生就是宽广，小时候向前看，现在往后看。他谈到在海流中游泳的经历，从紧张到放心，最后被海流带回家。对于在历史长河中的姿态，他希望是遗忘的姿态。
+# 访谈详细记录
+## 写作阶段与文学追求
+- 余华将文学创作分为1.0、2.0、3.0三个阶段：1.0阶段是逼自己坐下来写，让屁股和椅子建立友谊；2.0阶段受卡夫卡启发，写作越写越难，遇到心理表现障碍；3.0阶段受威廉·福克纳影响，采用视觉描写，让心脏停止跳动，让眼睛睁开。
+- 余华年轻时目标是对着托尔斯泰和陀思妥耶夫斯基去的，现在知道距离不可逾越，但这种野心支撑他一篇篇写下来，同时对自己的写作不满意。
+- 余华认为3.0版本以后就没再升级了，已经是大海；《活着》可能是4.0版，但对他已不是难题，因为写作已经很成熟。
+- 余华提到《十八岁出门远行》一天就写完了，6000字，对他这种写字比较慢的人已经是奇迹。
+## 作品创作与时代变化
+- 《兄弟》创作始于1996年，当时中国社会变化复杂；2003年和2004年重新写时，庆幸96年没有写完，因为2004年再看，96年时候的变化不算什么，那才是真正大的变化。
+- 余华认为最好的写作状态在40多岁到50岁，即《兄弟》到《第七天》期间，但那段时光被浪费，只出了两部作品。
+- 余华2006年开始写一部长篇小说，实践跨度与《兄弟》相同，从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写，写了一半没写完，现在身体状态可能还能维持激烈，但那个感觉没了。
+- 余华估计自己能够好好写作的时间可能还有十年左右，在三亚的工作就是写作、读书听音乐和锻炼。
+## 作品反响与批评应对
+- 《兄弟》出版时余华期待一片赞扬，结果一片骂声，他努力接受采访解释作品，但效果不佳；《第七天》出版时只接受了一个采访，让朋友做好挨骂准备，结果果然一片骂声；《文城》骂声少一些。
+- 余华对待批评的方式：第一不要看，第二有些批评要重视；有些批评没有道理，比如批评宋凡平太完美，但宋凡平是阶段性人物，只能写他在这个阶段的表现。
+- 余华认为《第七天》有批评说社会底层人未必都善良，这句话说得很好，会在以后写小人物时考虑进去，但《第七天》必须把善良在死无葬身之地表现出来，否则没有力量。
+## 网络热度与自我调节
+- 余华在互联网上看到关于自己的话有一半不是他说的，比如「想要命好的」「精神内耗，心里的戏太多」都不是他说的。
+- 余华曾停了一年活动，任何活动、采访都不做，进入冷静期；但自媒体时代会把几十年前的事情翻出来，以前说过的话都给你翻出来。
+- 余华面对中年危机，认为只有写作能得到新的东西，虚构的世界带来新的东西，现实世界每天都是重复的。
+- 余华自我调节方法：发生的事情无法选择，但可以选择什么让自己知道、什么让自己不知道，负面消息太多就屏蔽掉。
+## 文学理想与未来计划
+- 余华不再追求高度，追求宽度，认为作为作家能走到的高度就是现在的高度，允许自己下滑但不要下滑太多。
+- 余华认为这一代中国作家被马尔克斯误导，想在一本书里写一个世纪的故事，但没有能力在不到30万字的小说里写出一个世界。
+- 余华计划先写完一个喜剧，改变读者对他的印象，因为他的作品几乎都是悲剧，把悲伤留给虚构，把欢乐留给现实。
+- 余华希望下一步作品快一点完成，开学时与学生见面，处理学校事务后回三亚继续写作，安安静静把感觉找回来。
+## 人生感悟与历史姿态
+- 余华童年第一次看到大海，感受到宽阔辽阔，认为人生就是宽广；小时候人生感受是向前看，现在往后看，回忆占多了。
+- 余华在海流中游泳，从紧张害怕到放心，最后被海流带回家；他认为如果没有遇到海流，可能就回不来了。
+- 余华在三亚看到晚上的星空是童年的星空，因为这里没有污染，通过月光光晕发现月光是金色的，不是银色的。
+- 余华希望自己在历史长河中的姿态是遗忘的姿态，那些能够勉强被微风吹进耳朵的人也是勉强吹进来的。
+# 关键引语与金句
+&gt; “假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的，坐下来让屁股和椅子建立友谊，这是很重要的。”
+- 背景：谈文学创作1.0阶段时，回应如何开始写作的问题。
+&gt; “心理描写没有心理，它是视觉描写。”
+- 背景：谈3.0阶段受威廉·福克纳影响，以视觉描写呈现人物内心状态。
+&gt; “我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。”
+- 背景：回顾2006年开始写的一部长篇小说未能完成，感叹当年感觉已远去。
+&gt; “兄弟出版的时候，我认为肯定是一片赞扬……结果一片骂声弄得我有点糊涂。”
+- 背景：回忆《兄弟》出版时对反响的预期与实际遭遇的批评。
+&gt; “在互联网上，起码我看到的啊，关于我说的话，有一半不是我说的。”
+- 背景：谈到网络热度与自媒体时代，指出网上流传的许多话并非他本人所说。
+&gt; “发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。”
+- 背景：回应年轻人面对焦虑与负面消息如何排解的问题。
+&gt; “把悲伤留给虚构，把欢乐留给现实。”
+- 背景：谈到自己作品多为悲剧、计划先写一个喜剧改变读者印象时所说。
+&gt; “假如那个历史的长河里边有一个主题的话，这个主题就是遗忘。”
+- 背景：回应希望以什么样的姿态留在历史长河中，答以遗忘的姿态。</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>11212/3024</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="13.5" customHeight="1" s="9">
       <c r="A38" s="6" t="inlineStr">
@@ -13027,6 +13924,80 @@
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t># 讲座概况
+主讲人为会议中的发言人1，以对话访谈形式系统讲解柏林战役的历史背景、作战过程与影响，面向对二战史感兴趣的听众。讲解围绕五个板块展开：战役背景与双方兵力部署、战役过程与关键事件、英美未攻柏林的原因、战役细节与影视推荐、战役影响与后续历史。核心判断包括：柏林战役是人类历史上最大规模的城市作战，也是二战欧洲战场的最后一次大规模战斗；苏军以约250万兵力对德军约100万守军形成合围，自1945年4月16日发起进攻，至5月2日柏林德军投降、5月9日德国无条件投降；战役奠定了冷战欧洲部分的基调，德国自此分裂为东西两个德国直至1990年统一。关键锚点包括苏军距柏林60公里、英美联军距柏林100—120公里、希特勒于4月30日与妻子艾娃·布劳恩在地堡自杀。对听众而言，本讲有助于理解二战收尾阶段苏德双方的战略博弈、柏林战役的军事细节及其对战后欧洲格局的深远影响。
+# 核心观点与论证
+## 战役背景与双方兵力部署
+- **战役定位**：柏林战役是第二次世界大战欧洲战场的最后一次大规模战斗，也是苏德战争期间苏联和德国进行的最后一场大规模战役。
+- **战略态势**：1945年苏军进抵奥德河、尼斯河一线（今德国和波兰边境），距柏林仅60公里；英美联军才到达易北河一带，距柏林100–120公里，苏联已获先发制人机会。
+- **苏军部署**：白俄罗斯第一方面军（指挥官朱可夫元帅）从奥德河—法兰克福方向北部突击包围柏林；乌克兰第一方面军（指挥官科涅夫元帅）由克拉科夫及德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。
+- **德军兵力**：防守部队为中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（由老人和16岁以下孩子组成的民兵），总兵力约100万人，从柏林到桑多梅日桥头堡及奥德河一带布防。
+- **苏军兵力**：两个方面军总计约250万人，从北部什切青到南部德累斯顿形成合围网，对柏林实施合围。
+## 战役进程与关键节点
+- **第一阶段进攻**：1945年4月16日苏军以数以千计的火炮和卡秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击。
+- **推进受阻**：因德军在桑多梅日桥头堡修筑防线，苏军拖至4月20日左右才进抵柏林城区（今柏林潘科区及帕卡洛镇一带），4月24日白俄罗斯第一方面军突进柏林市区，科涅夫部队仍在向柏林边缘靠近。
+- **德军抵抗**：德军温克的第十二集团军与苏军一直进行周旋，是战役中表现突出的部队之一。
+- **希特勒自杀**：1945年4月30日，柏林已被苏军围死，红军距希特勒地堡仅两条街，希特勒不甘被俘，与妻子艾娃·布劳恩一起举枪自尽；此前4月29日二人举行了婚礼。
+- **战役结束**：4月30日夜间苏军占领德国国会大厦；5月2日经谈判，柏林城防司令魏德林宣布德军向苏军缴械投降，柏林战役结束；5月9日德国宣布无条件投降，二战欧洲部分正式结束。
+## 英美未攻柏林的原因
+- **战后协议约束**：丘吉尔曾想抢占柏林，但盟国事先已就战后德国地盘划分达成协议，柏林战后属于苏联，西方盟国只占西柏林区域。
+- **艾森豪威尔判断**：美军攻占柏林会增加不必要伤亡，且占领后仍需撤出，得不偿失；不如占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等德国精华地带。
+- **对苏需求**：打完德国后盟军还有求于苏联，需其共同对日作战。
+## 战役细节与影响
+- **易北河会师**：西欧部队与东边苏联部队事先没有交流，双方在易北河会师只是偶然，事先高层未达成共识，实为各打各的。
+- **红旗插上国会大厦**：著名照片中的红旗并非标准苏联制式军旗，而是士兵用床单和颜料临时绘制；插旗士兵手上戴有三块从德国老百姓抢来的手表，摄影师认为有碍国际观瞻，要求重新摆拍。
+- **战后格局**：柏林战役奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根一线，直至1990年两德统一。
+- **二战彻底结束**：日本于1945年9月2日在密苏里号军舰上签署无条件投降书，第二次世界大战彻底结束。
+# 金句总结
+&gt; “谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。”
+- 背景：解释苏联不惜代价强攻柏林的原因，占领柏林被视为战后至高荣誉。
+&gt; “这是人类历史上最大规模的城市作战。”
+- 背景：回应主持人关于柏林战役规模的确认，并引出城市作战与野外作战区别的讨论。
+&gt; “城市作战……敌人可能从任何地方攻击你的部队，你的坦克和汽车就在街上，敌人可能从建筑物或其他街道用火箭和机枪攻击，这非常困难和危险。”
+- 背景：用英文解释城市作战与野外作战的核心区别，强调城市环境中来自四面八方的威胁。
+&gt; “大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗。”
+- 背景：解释希特勒尸体被焚烧后外界说法不一、谣言盛起的原因，纳粹残余以自欺欺人方式继续抵抗。
+&gt; “与其这样，还不如说是尽可能去占领更多德国的精华地带……柏林就让给苏联吧。”
+- 背景：解释艾森豪威尔决定不攻柏林的原因，认为攻占柏林得不偿失，不如占领德国精华地带。
+&gt; “那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜，但是这个非常具有代表性的意义。”
+- 背景：补充红旗插上国会大厦这一标志性画面的细节，旗帜为士兵临时用床单绘制。
+&gt; “奠定了冷战欧洲部分的一个基调，就是差不多就是德国后来就分裂成了东西两个德国。”
+- 背景：回答柏林战役胜利后的世界格局，指出战役奠定了冷战欧洲基调并导致德国分裂。
+# Q&amp;A 环节
+**听众**：城市作战跟野外作战有什么明显区别或定义吗？
+**主讲人**：城市作战中部队在街道上，敌人可能从任何方向攻击，坦克和车辆在街道上容易被敌人用火箭筒和机枪从建筑或其他街道攻击，非常困难和危险。
+**听众**：是不是这个战役里面希特勒自杀了？
+**主讲人**：是的。1945年4月30日，柏林已被苏军围死，苏联红军离希特勒地堡仅两条街，希特勒不甘被俘，与妻子艾娃·布劳恩一起举枪自尽。
+**听众**：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么受关注？
+**主讲人**：因为自尽后部下用汽油焚烧其尸体，至今未见到遗体全貌，只获得烧焦的焦炭，外界说法不一，没有确切证据。除少数亲信外，大部分人坚信纳粹未覆灭，以自欺欺人的方式继续战斗，导致民间谣言盛行。
+**听众**：想更详细了解这个战役，有什么影视推荐吗？
+**主讲人**：苏联有《柏林战役》，德国有《帝国的毁灭》。
+**听众**：这两部影视在细节或倾向上有什么不同？
+**主讲人**：德国角度更多是希特勒最后生平及柏林防守的人事任命；苏联方面强调从高层到基层的描写，包括高层运筹帷幄和基层官兵舍生忘死。
+**听众**：主要进攻柏林的是苏联部队吗？
+**主讲人**：是的，同时还有半数波兰共产党的部队。
+**听众**：为什么英美不打柏林？
+**主讲人**：丘吉尔想抢占柏林，但盟国已达成战后占领区协议，柏林战后属苏联，西方盟国只占西柏林。艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤出，得不偿失，不如占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等精华地带。且盟军还有求于苏联共同对日作战。
+**听众**：这场战役大概持续了多久？
+**主讲人**：从4月16日开始，一直进行到5月2日。
+**听众**：有什么书可以看吗？
+**主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记中关于柏林战役后苏俄与西方博弈、西柏林划分和德国边境重新划定的内容。
+**听众**：柏林战役胜利后，当时世界形成了怎样的格局？
+**主讲人**：奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿今天的罗斯托克到南部图林根一带，直到1990年两个德国才统一。
+**听众**：B站上比较火的鬼畜片段就是这个战役末期发生的吗？
+**主讲人**：对，那个希特勒鬼畜片段出自电影《帝国的毁灭》，尤其是他大骂温克丢下柏林逃跑那一段。</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4609/3364</t>
         </is>
       </c>
     </row>
@@ -13172,6 +14143,70 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t># 全文摘要
+会议为多人自由讨论，共5位发言人参与，围绕社会规则合理性、理想工作形态、AI与机器人未来等话题展开。讨论覆盖四个板块：社会规则合理性、理想工作与AI替代劳动、机器人意识与人类控制、机器人军事应用与流行文化，最后简短提及语音分离标注测试。讨论以分享为主，未形成明确结论。
+# 分段速览
+## 00:00:02-00:01:40 社会规则合理性讨论
+发言人1提出必须买房、必须结婚等规则不合理，经济不好时更不可行；发言人2补充必须结婚生子，并认为结婚、买房、升职都取决于遇到的人和自身经济能力；发言人3认为人必须工作是合理的，发言人1补充工作合理但应做自己想做的、不与金钱挂钩。
+## 00:01:40-00:03:32 理想工作形态与AI替代劳动
+发言人2询问理想工作形态，发言人1表示希望每天按兴趣干活，发言人4提出不干活更好，发言人3举例宠物博主工作轻松可赚钱；发言人1指出总有些脏活累活无人承担，发言人3认为应让AI做苦活累活而非创作艺术，发言人2引用蔡明小品中机器人失控煮皮鞋汤的例子，讨论机器人替代劳动后人类幸福感是否提升。
+## 00:03:32-00:07:14 机器人意识与人类控制
+发言人2担心机器人有独立意识后不受人类控制，可能像终结者中那样反抗并奴役人类，或成为犯罪代理人、职业杀手、超级战士，反抗后果灾难性；发言人5认为机器人只需执行命令无需思想，发言人3认为智能和思想可能无法分开，发言人5担心思想会带来负面影响，如执行指令时伤人。
+## 00:07:14-00:09:54 机器人军事应用与流行文化
+发言人2提到军队已有单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人状态，发言人3确认排雷机械狗和机械车已在应用；随后讨论游戏《重返德军总部》中的超级战士和数码宝贝中的机械邪龙兽等流行文化中的机器人形象，并提及数码宝贝第二部第七集安徒路兽通过人脸识别判断身份的剧情。
+## 00:09:54-00:10:56 语音分离标注测试与结束
+发言人3提到语音分离测试中同时两人以上说话会有问题，发言人1询问两人一起说话标注情况，认为标注人需认识声音，并认为单人麦很强；随后发言人3提议结束，大家同意。
+# 要点梳理
+## 社会规则合理性讨论
+- **发言人1**：必须买房、必须结婚等规则不合理，经济好的时候可以，经济不好的时候不太可以。
+- **发言人2**：必须买房、必须结婚生子等规则取决于遇到什么样的人，也取决于自身经济能力，不能说得太绝对。
+- **发言人3**：人必须工作是合理的。
+- **发言人1**：工作合理，但应做自己想做的，不要与金钱挂钩太紧密。
+## 理想工作形态与AI替代劳动
+- **发言人1**：理想工作是每天起来想干啥就干啥，按自己兴趣干活。
+- **发言人4**：提出有没有可能不干活更好。
+- **发言人3**：举例宠物博主工作好，每天发宠物视频、剪视频就能赚钱。
+- **发言人2**：补充游戏高手也是类似工作。
+- **发言人1**：指出总有些脏活累活没人愿意承担。
+- **发言人3**：认为应让AI做苦活累活，而不是让AI搞创作、艺术。
+- **发言人2**：引用蔡明小品中机器人失控、把牛皮制品手表皮鞋煮汤的例子，讨论机器人替代劳动后人类幸福感是否更高。
+- **发言人1**：认为机器人负责生产、人负责享受挺好，但质疑这种规则能否实现。
+- **发言人2**：认为AI普及并普惠到实体后，只要人类控制得当，人类或可不用干苦活累活。
+## 机器人意识与人类控制
+- **发言人2**：担心机器人有独立思想意识后不受人类控制，像《终结者》中那样罢工、反抗并奴役人类。
+- **发言人3**：提到斯皮尔伯格的人工智能电影也是类似结局，归结为哲学问题。
+- **发言人5**：认为机器人只要能接受命令、执行命令即可，不必有思想。
+- **发言人3**：认为机器人得有智能，但智能和思想可能无法分开。
+- **发言人5**：担心机器人有思想会带来不好影响，如执行指令时打人。
+- **发言人2**：认为机器人可能成为犯罪代理人、职业杀手或超级战士，独立意识群体罢工后反抗后果灾难性。
+- **发言人2**：提到军队已有单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人状态，若列装普及或不再需要单兵轻武器。
+- **发言人3**：确认排雷机械狗和机械车已在应用。
+## 流行文化中的机器人形象
+- **发言人2**：提到游戏《重返德军总部》中的超级战士，以及数码宝贝中守卫兽、机械装甲兽升级进化为安多路兽。
+- **发言人2**：数码宝贝第一部最终boss机械邪龙兽是一台精密机械式超级计算机形成的生命体，专为破坏而存在。
+- **发言人2**：数码宝贝第二部第七集中安徒路兽被黑色魔轮控制后，仍能通过人工识别和人脸识别判断身份，主角嘉儿通过记忆和回忆唤醒其最终记忆。
+## 语音分离标注测试
+- **发言人3**：提到语音分离测试，同时两人以上说话会有问题。
+- **发言人1**：询问两人一起说话的标注情况，认为标注人需要认识声音。
+- **发言人1**：认为单人麦很强。
+- **发言人3**：提议结束，大家同意。
+## 待确认与风险
+- **机器人有独立意识后可能不受人类控制**：发言人2提出机器人可能罢工、反抗并奴役人类，后果灾难性。
+- **机器人有思想可能带来负面影响**：发言人5担心机器人执行指令时可能伤人。
+- **机器人可能成为犯罪代理人、职业杀手或超级战士**：发言人2提出这一风险。
+- **语音分离标注测试可行性**：同时两人以上说话时标注存在问题，标注人需认识声音，是否可行未确认。</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3931/2354</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="13.5" customHeight="1" s="9">
       <c r="A40" s="6" t="inlineStr">
@@ -13259,6 +14294,67 @@
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t># 全文摘要
+会议为两人参与的开放式讨论，由发言人1主导、发言人2补充提问，围绕哥斯拉系列电影剧情展开，并延伸至核废水排放的现实影响。讨论覆盖哥斯拉系列历史与日美版本剧情、角色设定、哥斯拉与奥特曼的关系，以及日本核废水排放对健康与食品选择的影响、切尔诺贝利事件对比等板块。哥斯拉首部电影诞生于1954年，起源为海底生物吸食核废料变异，在日本神话中是大自然的守护神；美国版《哥斯拉大战金刚》中机械基多拉由基多拉残骸加装机械装甲制成，2016年日本版《新哥斯拉》中哥斯拉最终被冷冻封印。讨论以分享为主，未形成明确结论。
+# 分段速览
+## 00:00:00–00:09:18 哥斯拉系列电影剧情梳理
+发言人1主导梳理哥斯拉系列电影的历史与剧情线，从1954年首部电影讲起，介绍哥斯拉起源为海底生物吸食核废料变异而成，在日本神话中是大自然守护神，攻击人类源于人类破坏生态。随后展开美国版三部曲剧情：2014年《哥斯拉》中哥斯拉与人类携手消灭雾托；《怪兽之王》中基多拉降临地球，人类试图用水下爆炸使哥斯拉窒息，反被基多拉干扰，最终人类重新以核武器唤醒哥斯拉击败基多拉；《哥斯拉大战金刚》中反派残余势力将基多拉残骸加装机械装甲制成机械基多拉，金刚与哥斯拉联手将其打败。日本版剧情更复杂，2016年《新哥斯拉》中哥斯拉不断升级，最终被无人机投放炸弹耗能后以冷冻剂封印。发言人2偶尔补充提问。
+## 00:09:18–00:10:51 哥斯拉与奥特曼关系讨论
+发言人1说明哥斯拉与奥特曼导演同为圆谷英二，但分属不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星，且两者均为正面形象，未同台战斗。翼龙拉顿作为反派在哥斯拉与奥特曼作品中均与正派形象战斗过。发言人2补充说明哥斯拉是哥斯拉系列中的反派角色。
+## 00:10:51–00:12:01 衍生电影与系列持续原因
+发言人2提及哪吒大战变形金刚的中美合拍电影，发言人1确认确有此事。发言人1总结哥斯拉系列从1954年至今的演变脉络，指出该IP持续推出的原因在于哥斯拉每次未被真正消灭、沉睡后复活，形成不同版本续集；并认为只要日本不停止排放核废水，此类题材就不会停。
+## 00:12:01–00:15:17 核废水现实影响与切尔诺贝利对比
+讨论由哥斯拉题材引申至日本核废水排放的现实问题。发言人2回忆在日本留学期间因核废水排放购买中国进口的鱼，并指出日本国产食品因民族自信价格昂贵。发言人1提出核废水可能导致白血病等病变，但未出现类似哥斯拉的变异。随后对比切尔诺贝利核电站已用水泥封存、成为鬼城、方圆百里无人区，认为日本排放核废水更不负责任。发言人2提及使命召唤4游戏中切尔诺贝利关卡，随后宣布讨论结束。
+# 要点梳理
+## 哥斯拉系列电影剧情讨论
+- **哥斯拉起源**：首部哥斯拉电影诞生于1954年，迄今约70多年；起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
+- **哥斯拉神话定位**：在日本神话中是大自然的守护神，攻击人类是因为人类无限制搞核试验、破坏大自然生态。
+- **系列扩展题材**：人类频繁战争和核试验唤醒沉睡生物、招致外星生物入侵；有时哥斯拉作为守护神与人类携手打败其他怪兽和外星生物。
+- **《哥斯拉怪兽之王》**：反派基多拉为外星生物中的龙头老大角色。
+- **《哥斯拉大战金刚》**：基多拉被哥斯拉打败后，人类反派势力将基多拉仅存的一个脑袋残骸加装机械装甲复合升级为机械基多拉，金刚与哥斯拉不计前嫌联手将其打败；战斗场景发生在香港九龙。
+- **摩斯拉设定**：日本神话中还有一只蝴蝶叫摩斯拉，负责给哥斯拉疗伤。
+- **哥斯拉正反派形象**：既有作为反派出现的印象，也有作为正面形象出现的情况；当基多拉降临地球时，哥斯拉与人类携手对抗。
+- **2004年日本版《哥斯拉最后的战斗》**：有中国演员章子怡参演。
+- **系列续集逻辑**：哥斯拉每次都没被真正打败、杀死和消灭，重新沉睡后复活，因此能持续推出不同版本的续集。
+- **金刚与哥斯拉冲突原因**：金刚领地为热带雨林，哥斯拉领地为海洋；海洋把热带雨林淹了，双方因地盘起冲突。
+### 美国版剧情线
+- **1954年首部**：拍完后收视率不太被认可、偏低。
+- **2014年美国版《哥斯拉》**：另外两个物种（蝙蝠类变异体）以核弹、核废料为能源食物，名为雾托；哥斯拉为维护地球安全与人类携手将雾托团灭。
+- **第二部《怪兽之王》**：人类频繁进行核武器实验唤醒全世界沉睡的怪兽，基多拉降临地球；人类试图用水下子母弹和核试验形式让哥斯拉在水里窒息死亡，但基多拉是外星物种、武器对其无效，哥斯拉差点被溺死在海里；后来人类重新给哥斯拉喂核废料、核武器实爆将其唤醒，打败基多拉。
+- **第三部《哥斯拉大战金刚》**：反派残余势力不甘心基多拉败亡，将基多拉仅存的有意识的头加装机械装甲，金刚挺身而出与哥斯拉联手解决。
+- **福原博士**：曾表示不能用对付基多拉的办法（核武器）来对付它，因为是外星生物、没有用；人类差点成猪队友，基多拉没事、哥斯拉差点被误杀。
+### 日本版剧情线
+- **早期日本版**：哥斯拉最早作为怪兽出场；翻拍剧情与美国版类似，但人类反派做成外星人形象，外星人控制基多拉和其他怪兽；哥斯拉因基因与其他怪兽不同，反杀外星人控制的怪兽、重新解放地球。
+- **2016年《新哥斯拉》**：海里蜥蜴类生物喝核废水后不断壮大，吸收核废料后升级变大；人类各种武器攻击不仅无效反而增强其战斗力和战斗形态；最终以无人机投放炸弹方式耗光能量，再用冷冻剂封印。
+### 哥斯拉与奥特曼关系
+- **导演渊源**：哥斯拉与奥特曼最早都是导演圆谷英二的作品，但属于不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星，两者未同台。
+- **正派形象**：两者都是正面形象，无法直接战斗。
+- **拉顿**：会飞的翼龙/鸟，在哥斯拉和奥特曼不同作品中都与正派形象战斗过。
+### 哪吒大战变形金刚
+- **电影传闻**：有《哪吒大战变形金刚》电影，据称中美合拍、已开拍，发言人1表示等拍出来再看。
+## 核废水排放的现实影响
+- **题材延续原因**：只要日本不停止排放核废水，哥斯拉这类题材永远都不会停。
+- **日本排放决策**：日本认识到问题但决定权不在自己，美国叫排不敢不排。
+- **核废水变异风险**：万一有生物因核废料发生病变变异，谁也说不清楚。
+- **日本食品进口政策**：前段时间不让进口日本食品，现在已放开。
+- **发言人2留学经历**：在日本留学期间因日本开始排核废水，吃的鱼都买中国进口到日本的鱼；中国进口的鱼相对便宜。
+- **日本国产食品价格**：日本有民族自信，产品打上国产标签就非常贵，即使品质一般。
+- **核废水健康影响**：目前没看到变异，但肯定有得各种白血病等病变的；不会像哥斯拉那样喝了核废料马上变异成庞然大物。
+- **切尔诺贝利对比**：切尔诺贝利核电站反应堆已用水泥封住，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里无人区；相比日本核废水排放更负责任，至少拦截封存了。
+- **切尔诺贝利生物变异**：当地生物长得奇怪、畸形，但没说变强。
+- **相关游戏内容**：使命召唤4「双狙人」关卡中，车臣叛军去切尔诺贝利挖核废料，被英国SAS特种部队主角狙杀，只打断一条胳膊。</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5319/3060</t>
         </is>
       </c>
     </row>
@@ -13494,6 +14590,64 @@
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为6位发言人（编号1至6）围绕“18岁以前的深刻印象和记忆”展开的分享型讨论，由发言人1发起话题，成员依次分享个人经历。讨论以漫谈发散方式推进，先后涉及逃课与网吧游戏记忆、阅读与漫画（郭敬明小说、柯南、老夫子、意林等）、电脑游戏流行趋势（摩尔庄园、穿越火线、地下城与勇士、仙剑、魔兽争霸等）、第一人称射击游戏及其暴力内容（求生之路、生化危机等），并延伸至游戏与电影关系、美国政府疫情表现等评论。整体以分享观点为主，未形成统一结论。讨论中提及多个时间与专名锚点，如2008年国服开服的穿越火线、2020年新冠疫情后求生之路重新火爆、Steam要求18岁以上注册等。
+# 发言要点
+## 18岁前的逃课与游戏记忆
+- **发言人1**：初中走读，每周一下午4点放学后去游戏厅、网吧，流行游戏包括穿越火线（CF）、反恐精英online（CS online）、使命召唤、战地、魔兽等；高中因高考压力不敢逃课，转而追星和搞乐队，喜欢朋克金属音乐。
+- **发言人2**：18岁前没逃过课，大学逃过一次。
+- **发言人3**：认为逃课是正常现象。
+- **发言人4**：补充上大学逃课不算。
+## 18岁前的阅读与漫画记忆
+- **发言人5**：特别喜欢郭敬明的小说。
+- **发言人2**：提到郭敬明小说《梦里花落知多少》，表示看着难受；当时喜欢看漫画，也看意林、读者、故事会等杂志。
+- **发言人4**：班上流行看柯南。
+- **发言人1**：流行看柯南和老夫子，老夫子是香港漫画。
+- **发言人5**：提到萌化三国。
+## 18岁前的电脑游戏流行趋势
+- **发言人4**：提到摩尔庄园、赛尔号。
+- **发言人2**：提到穿越火线、地下城与勇士；初中玩魔兽争霸，区分魔兽争霸（单机）和魔兽世界（网游）。
+- **发言人1**：提到单机游戏求生之路，联机局域网玩。
+- **发言人5**：玩过仙剑四；提到英雄联盟、DOTA，并讨论鄙视链。
+- **发言人2**：认为王者荣耀在鄙视链最低端。
+## 第一人称射击游戏与暴力内容讨论
+- **发言人1**：曾因在贴吧和QQ空间写文章骂穿越火线被平台封禁，后成为CS反恐精英铁杆粉，喜欢僵尸模式；被舞蹈队说跳舞姿势像舞体僵尸。
+- **发言人5**：质疑游戏暴力且无年龄限制，认为同龄人很少玩这类游戏。
+- **发言人1**：解释求生之路第二部血腥暴力，导致Steam要求18岁以上才能注册；认为制作团队精准预测美国政府疫情表现，2020年新冠疫情后游戏重新火爆。
+- **发言人1**：描述求生之路剧情——美国政府默不作声、军队暴力清理、主角自救；主角团是无症状感染者，被狂暴病毒感染人群攻击。
+- **发言人2**：提到欧美玩家热衷打僵尸游戏，欧洲年轻人都在打僵尸。
+- **发言人1**：提到生化危机也是病毒泄露、政府反应迟钝，生化三用核武器夷平城市。
+## 游戏与电影关系及衍生讨论
+- **发言人1**：指出生化危机先有游戏后有电影；求生之路基于惊变48小时和生化危机，先有电影后有游戏。
+- **发言人1**：认为变形金刚先有玩具，后有MV和电影，提到绿日乐队（Green Day）的MV。
+- **发言人3**：喜欢玩塔防游戏，如植物大战僵尸、Kindle rush。
+- **发言人2**：提到植物大战僵尸有变态版，后期满屏子弹导致电脑卡顿。
+- **发言人1**：评论使命召唤黑色行动基于冷战时期美苏真实历史，现代战争虚构，认为高估俄罗斯。
+# 共识形成
+- **一致意见**：与会者普遍认同18岁前的记忆以游戏、漫画、小说等娱乐活动为主，且逃课、去网吧等行为在当年属常见现象；对《求生之路》制作团队精准预测美国政府疫情表现、2020年疫情后游戏重新火爆这一判断，发言人1、发言人6等均表示认可，发言人6以「艺术源于生活」作呼应。
+- **倾向性认识**：在游戏暴力与年龄限制问题上，发言人5质疑「那个游戏没有什么年龄限制」「特别暴力，那小孩能玩吗」，发言人1回应称《求生之路》第二部因血腥暴力，Steam要求18岁以上才能注册账号，双方对游戏暴力程度及限制必要性认识一致。
+- **主要分歧点**：在游戏鄙视链排序上，发言人5提出英雄联盟、DOTA、王者荣耀间存在鄙视链，发言人2认为「王者荣耀就是更低最低最低」，发言人1未明确表态，仅以「鄙视要最底端」回应，未形成统一结论；在《变形金刚》起源上，发言人4提问先有电影还是先有玩具，发言人1明确回答「先有的玩具，后来有的MV和电影」，发言人2未提出异议，但该结论仅由发言人1单方给出，未获全体确认。
+# 待探讨问题与后续
+- **未确认**：发言人5质疑《求生之路》等游戏暴力且无年龄限制，认为同龄人很少玩，发言人1解释Steam要求18岁以上才能注册，但未确认该限制的实际执行情况。
+- **未确认**：发言人1称《求生之路》制作团队精准预测美国政府疫情表现，2020年新冠疫情后游戏重新火爆，此说法为个人观点，未获其他成员验证。
+- **未确认**：发言人1认为《使命召唤：现代战争》剧情高估俄罗斯军队在乌克兰的表现，属个人评论，未展开讨论。
+- **未确认**：发言人2提到《植物大战僵尸》有变态版，后期满屏子弹导致电脑卡顿，未确认具体版本名称。
+- **未确认**：发言人1称自己曾因在贴吧和QQ空间写文章骂穿越火线被平台封禁，未提供具体时间与证据。
+- **未确认**：发言人5提到《萌化三国》，未展开说明具体内容。
+- **未确认**：发言人2提到《魔兽争霸》与《魔兽世界》的区别（单机与网游），未深入讨论。
+- **未确认**：发言人5提到英雄联盟、DOTA与王者荣耀存在鄙视链，发言人2认为王者荣耀在最低端，未达成一致。</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6453/2396</t>
         </is>
       </c>
     </row>
@@ -13763,6 +14917,105 @@
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论为四人（发言人1至发言人4）围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说的自由漫谈，以分享观点为主，未形成统一结论。讨论由发言人2提议继续此前未完成的《红楼梦》话题开场，随后依次谈及《红楼梦》的官场暗线与四大家族兴衰、护官符诗句、冷香丸制作细节、薛宝钗结局版本争议及朝代与作者问题；《金瓶梅》与《水浒传》的武松报仇线差异、西门庆结局与人物发展史；《西游记》中佛教虚伪情节；以及孙权二宫之争等历史话题。讨论整体呈漫谈发散式推进，各议题间由发言自然衔接，未按预设议程逐块展开。
+# 发言要点
+## 《红楼梦》讨论
+- **发言人3**：《红楼梦》有一条官场暗线，四大家族兴衰与官场地位相关，如王熙凤前期地位高、后期结局惨，与其兄长在官场上的地位变化相关。
+- **发言人4**：质疑四大家族人数少，每家就两家人多一点，只知典型人物，如王家登场人物少、薛宝钗家没什么靠山。
+- **发言人3**：回应薛宝钗家是做生意的，主要是有钱。
+- **发言人1**：补充四大家族护官符诗句——贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁。
+- **发言人4**：认为护官符说得很厉害，但实际感觉没什么厉害人家。
+- **发言人3**：指出四大家族整体都在走下坡路。
+- **发言人1**：认同，认为说的就是王朝家族的衰败。
+- **发言人4**：回忆小时候看《红楼梦》没看明白，但记得江南吃螃蟹非常讲究，要卸钱卸身，第一次听说吃螃蟹需要这么多工具。
+- **发言人3**：提到薛宝钗的冷香丸制作讲究，需要雨水那一日的雨水、小雪那一日的雪，每个节气都要正好碰上。
+- **发言人1**：补充冷香丸配方——春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
+- **发言人3**：提及薛宝钗结局有版本争议——120回版本中她嫁给贾宝玉，但贾宝玉不久就出家，好多人说是无性婚姻；另有一个版本说她后来怀了一个孩子。
+- **发言人2**：追问怀的孩子是不是贾宝玉的。
+- **发言人3**：承认那是狗血版本。
+- **发言人1**：认为应该不至于弄这么狗血。
+- **发言人2**：指出有人把《金瓶梅》和《红楼梦》混淆。
+- **发言人3**：指出《红楼梦》没有明确朝代，是写得很虚的故事。
+- **发言人4**：认为作者是那个时代的，就是映射那个时代。
+- **发言人2**：追问《红楼梦》在历史上有没有真实发生的历史事件。
+- **发言人1**：指出《红楼梦》当时是禁书，不说朝代已经是禁书了，说朝代更禁。
+- **发言人4**：提到有说法称《红楼梦》很明显在映射当时时代，也有人说是曹雪芹的经历，他以前好像是个大家族。
+- **发言人3**：认为要不然作者写不出那么多细节。
+- **发言人4**：补充写不出吃螃蟹的技巧。
+- **发言人1**：认同，认为冷香丸一般人怎么想不出来。
+## 《金瓶梅》与《水浒传》讨论
+- **发言人1**：讲述《金瓶梅》中武松报仇未成功的情节——武松去找西门庆时，西门庆在楼上喝茶，仆人报信后他从楼上翻下逃走，与《水浒传》中直接砍头不同；武松后被发配，故事开始讲西门庆的线。
+- **发言人4**：认为《金瓶梅》比《红楼梦》接地气一点。
+- **发言人2**：询问《金瓶梅》后来讲的什么。
+- **发言人4**：问《金瓶梅》背后是不是让武松打死的，认为金瓶梅里没有武松的事儿。
+- **发言人1**：说明《金瓶梅》从杀了武大郎之后开始写。
+- **发言人3**：确认《金瓶梅》有报仇线。
+- **发言人1**：补充有报仇线但没报仇成功，所以很真实，和水浒在一块写。
+- **发言人4**：提到西门庆最后死是因为重病昏过去。
+- **发言人2**：总结西门庆霸凌武大郎，被高官和大家族的权势摁压下来。
+- **发言人1**：补充《金瓶梅》里武松报仇总是被打压下去，无论官职还是财富地位都不如西门庆。
+- **发言人2**：询问西门庆和宋江等人有没有交集。
+- **发言人3**：认为应该不会写，但丞相是同一个丞相。
+- **发言人4**：提到西门庆最后跟童贯还是谁攀上线，跟中央攀上关系，成为当地一霸。
+- **发言人2**：追问宋江起义是否成功。
+- **发言人3**：认为《金瓶梅》就是西门庆这个小人物的发展史，展现官场黑暗——西门庆这样一个无赖能爬到比较高、过得比较舒服。
+- **发言人4**：提到《金瓶梅》里吃的也写得很好，西门庆摆宴。
+- **发言人2**：询问《金瓶梅》里有没有像《水浒》那样的起义章节。
+- **发言人3**：确认没有，就是从西门庆这个小人物的发展史来写。
+- **发言人2**：询问西门庆结局在两个版本里分别是什么样。
+- **发言人3**：说明《水浒传》里西门庆被武松砍头，《金瓶梅》里西门庆因过度纵欲而死。
+- **发言人2**：询问宰相或丞相的结局。
+- **发言人3**：表示只看了一点，没看到。
+- **发言人4**：表示忘了。
+- **发言人4**：问潘金莲在《金瓶梅》里属于什么。
+- **发言人3**：提到西门庆有十个老婆，有的老婆特别懦弱，潘金莲属于很有心机、比较强势的那一种。
+- **发言人4**：确认潘金莲属于强势类型。
+- **发言人4**：问《金瓶梅》里有没有武大郎这个人，武大郎是不是也死在潘金莲手下。
+- **发言人3**：确认前面应该还是差不多，武大郎也是死在潘金莲手下。
+- **发言人3**：补充记得西门庆有一个老婆死于迷信——生病了去看和尚，不去治病，信这个，回来死了。
+- **发言人3**：提到《金瓶梅》里佛教也可黑，收灯油钱。
+- **发言人2**：确认《金瓶梅》和《水浒传》是北宋时期的故事，与《红楼梦》不同朝代。
+- **发言人4**：确认《红楼梦》是明清的，明末清初。
+- **发言人2**：总结《水浒》与《金瓶梅》是平行的，《红楼梦》是单独的故事线。
+- **发言人3**：确认不是一个朝代。
+## 《西游记》及其他讨论
+- **发言人1**：提到《西游记》里如来佛祖说天庭派人帮一个国家，帮完之后如来佛祖说区区收了300两黄金，体现佛教虚伪。
+- **发言人2**：追问是哪个章节。
+- **发言人1**：表示忘了，好像是最后一集。
+- **发言人2**：补充《西游记》佛教虚伪的例子——孙悟空和唐僧单独取经时寄宿寺院，住持有很多袈裟，贪图唐僧袈裟，后来引火把自己烧死。
+- **发言人4**：提到黑神话里的相关内容。
+- **发言人1**：补充还有金齿蟑螂。
+- **发言人2**：引出孙权二宫之争——长子孙和与太子孙登之争，不同大臣支持不同儿子，孙权的老婆王夫人特别有心机，和孙鲁班一起反杀，把东吴政局搅得一团糟。
+- **发言人3**：表示对二宫之争了解不多。
+- **发言人1**：提示时间差不多，提议再起一条，暂停当前讨论。
+# 共识形成
+- **一致意见**：与会者普遍认可《红楼梦》存在一条官场暗线，四大家族兴衰与官场地位相关，如王熙凤地位与其兄长在官场上的地位相关，其结局悲惨也与兄长先死有关；同时认为四大家族整体处于下坡路，对应王朝家族的衰败。
+- **倾向性认识**：关于《金瓶梅》，多数发言倾向认为该书是西门庆这个小人物的发展史，展现官场黑暗——西门庆作为无赖能爬到较高位置；武松报仇线在《金瓶梅》中未成功，与《水浒传》中直接砍头不同，西门庆在《金瓶梅》中因过度纵欲而死。
+- **主要分歧点**：关于薛宝钗结局，发言人3提到120回版本中她嫁给贾宝玉后贾宝玉不久出家，有说法称无性婚姻，另有版本称她后来怀了孩子；发言人1认为「不至于弄这么狗血」，发言人2质疑孩子是否为贾宝玉的，发言人3回应那是「狗血版本」。
+- **结论口径**：发言人3指出《红楼梦》没有明确朝代，是虚构故事；发言人4提到有说法称其映射当时时代或曹雪芹个人经历；发言人1补充《红楼梦》当时是禁书，因此不敢写明朝代。
+# 待探讨问题与后续
+- **未确认**：《红楼梦》中四大家族是否真的只有几个人，发言人4质疑「四大家族感觉就没几个人呀，每家都两家人还多一点」，发言人3回应「那可能是咱没看书啊，书里是不是人挺多呀」，未达成一致。
+- **未定论**：《金瓶梅》中西门庆的结局在不同版本中是否一致，发言人2询问「西门庆的结局在这两个版本里面都是什么样子的」，发言人3回应「在金瓶梅的版本是终于过度死」，发言人1补充《水浒传》中武松直接砍头，但未确认版本细节。
+- **未确认**：《红楼梦》是否映射曹雪芹个人经历，发言人4提到「有这种说法不知道您知道」，发言人3回应「要不然他写不出来那个那么多的细节」，未形成定论。
+- **未确认**：《金瓶梅》中潘金莲是否最有心机，发言人3表示「我印象中是这样」，发言人4未明确回应，细节记不清。
+- **待核实**：《西游记》中如来佛祖收300两黄金的具体章节，发言人1表示「那是哪一集啊？忘了忘了，好像是最后一集吧」，未确认具体出处。
+- **待核实**：《金瓶梅》中西门庆与宋江起义是否有交集，发言人2询问「西门庆后来和什么宋江这些人有没有什么交集」，发言人1回应「理亏不知道了」，发言人3表示「应该不会写」，未核实。
+- **未定论**：《金瓶梅》中武松报仇线是否成功，发言人1讲述武松报仇被高官权势打压、被发配，发言人3确认「有报仇线，但是没有报仇成功」，但未讨论后续发展。
+- **未确认**：《红楼梦》中薛宝钗结局版本争议，发言人3提到120回版本中贾宝玉出家、有说法称无性婚姻，另有版本称她后来怀了孩子，发言人1回应「这个应该不至于弄这么狗血」，未达成一致。
+- **未提及**：原文未提及任何后续分工或约定。</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5893/4046</t>
         </is>
       </c>
     </row>
@@ -14046,6 +15299,55 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t># 全文摘要
+会议为多人闲聊与话题讨论，参与者为六位发言人，无明确主办方或机构背景。前半段围绕个人阅读与综艺观看展开，发言人1提到反复阅读《红楼梦》，高中时读不懂、反复读才发现有意思；发言人2和4表示不常看小说，更常看短剧和综艺。发言人1介绍综艺《种地吧》，称节目有十个男孩，录制周期半年、24小时录制，成员成立农业公司，种植小月季和水培蔬菜，项目有亏有盈；还提到英国综艺《克拉克森的农场》。闲聊中涉及专业背景：发言人2为俄语专业但就业未从事相关职业，发言人1学数学后学统计，发言人4学软件工程。后半段发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法，发言人5表示对此话题不懂，讨论未深入，因设备与人员安排中断。以分享为主，未形成明确结论。
+# 分段速览
+## 00:00:02–00:06:23 闲聊：阅读、综艺与专业背景
+会议开场为多人闲聊。发言人1提到反复阅读《红楼梦》，高中时读不懂，反复读才发现有意思；发言人2和4表示不常看小说，更常看短剧和综艺。话题转向综艺，发言人1介绍《种地吧》，称节目有十个男孩，录制周期半年、24小时录制，成员成立农业公司，种植小月季和水培蔬菜，项目有亏有盈；还提到英国综艺《克拉克森的农场》。随后聊到专业背景：发言人2为俄语专业但就业未从事相关职业，发言人1学数学后学统计，发言人4学软件工程。
+## 00:06:23–00:10:22 闲聊：俄语专业与护发话题
+发言人2提到自己是俄语专业，但就业时未往俄语方向走，因五六年未用已遗忘；谈及俄罗斯人在华贸易生意，称内部消化较多、对外营销较少。随后话题转向护发，发言人4分享洗发水换着用的习惯，称目前囤有三种，换用后头发不易油痒；发言人2询问品牌，发言人4表示需查订单后告知。
+## 00:10:22–00:13:02 日本现代化转型话题与设备调整
+发言人5与6接续录制，发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法，发言人5表示对此话题不懂。因设备与人员安排（八爪鱼、原厂人员等）需调整，讨论未深入即中断，发言人1前往三楼找会议室，录制暂告段落。
+# 要点梳理
+## 个人阅读与综艺观看
+- **《红楼梦》阅读**：发言人1表示看过很多遍，高中时作为推荐读物初读不太能读懂，反复读之后才发现有意思。
+- **阅读习惯对比**：发言人2表示不怎么看小说，刷短剧更多；发言人4同样表示不常看小说。
+- **综艺偏好**：发言人2看电视剧和综艺较多，发言人4也以娱乐综艺为主，烧脑类内容看得少，认为工作已够费脑、休息时间宝贵。
+- **综艺类型**：发言人4偏好旅游类和户外类综艺，发言人2提到做饭类综艺。
+- **《种地吧》节目**：发言人1看过一段时间，节目有十个男孩，走偶像路线但选择小众路径，大部分成员搞音乐，后来组成组合并开演唱会，粉丝较多。
+- **《种地吧》录制模式**：几乎一天24小时录制，一录录半年，视频素材特别多；十人因综艺组到一起并形成绑定。
+- **《种地吧》农业经营**：成员成立农业公司，尝试创业发展新型农业；种植小月季和水培蔬菜，投多个项目，有的亏钱有的盈利。
+- **《种地吧》股东结构**：十人是实际股东，每人掏钱参与，节目可能另有收益。
+- **《种地吧》收益来源**：个人挣钱主要靠综艺，节目内以农业主题讲农业怎么挣钱；最近三农主题内容较多，挺多人喜欢看。
+- **《种地吧》养殖情况**：有一个鱼塘，可能里面有鱼，但没有认真去做养殖这件事。
+- **农业门槛**：种月季需要请专门的人看水和看土，外行人很难操作。
+- **《克拉克森的农场》**：发言人1提到英国种地综艺，认为也挺好看。
+## 专业背景与职业
+- **发言人2专业**：俄语专业，但就业时未往俄语方向就业，五六年没用已忘记。
+- **俄语使用场景**：发言人2认为北方可能能用上，比如做贸易。
+- **俄罗斯人贸易信息**：发言人2提到康鹏曾科普俄罗斯人贸易相关内容，但称不怎么外传，内部消化较多，对外营销做得比较少。
+- **发言人1专业**：之前学数学，后来学统计，一直是理科生。
+- **发言人4专业**：理科生，学软件工程，属工科。
+## 闲聊杂谈
+- **音色辨识**：发言人1认为三人音色不太像，应该容易分开。
+- **洗发水使用**：发言人4换着用洗发水，家里囤有三种轮着用，之前用一款容易油或痒就换，现在确实没那么容易油了。
+- **洗发水推荐**：发言人2询问推荐，发言人4未给出具体品牌，称用的牌子不认识、叫不来，答应找订单后告知。
+## 日本现代化转型
+- **议题提议**：发言人6提议讨论日本现代化转型，涉及明治维新与和平宪法。
+- **发言人5回应**：表示对此话题不懂。
+- **讨论中断**：因设备与人员安排（八爪鱼、金融相关事务、三楼会议室等）讨论未深入，发言人6称「彪子在日本上学是主场」但未展开。</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5310/2031</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="13.5" customHeight="1" s="9">
       <c r="A44" s="6" t="inlineStr">
@@ -14195,6 +15497,99 @@
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t># 讲座概况
+主讲人系统讲解了朝鲜半岛从分裂到统一再到二战后分裂的历史脉络，重点围绕朝鲜战争展开，并面向听众解答了关于半岛现状、旅游、军队战斗力等疑问。讲座覆盖朝鲜战争爆发背景、主要战役进程、停战协定及战后影响、朝韩分裂原因、抗美援朝决策缘由等板块。核心判断包括：朝鲜战争奠定中国强国地位，美国在越南战争中未敢越过北纬十七度线；朝韩仅名义停战，三八线悲剧延续至今；若朝韩统一大概率是韩国兼并朝鲜，但可能成为东北亚不稳定因素。关键锚点包括1950年6月战争爆发、1953年7月27日停战协定、三八线及金刚山地区。讲座对理解朝鲜半岛历史与当前东北亚局势具有参考意义。
+# 核心观点与论证
+## 朝鲜战争爆发背景与进程
+- **三八线形成**：1945年二战结束、日本投降后，美苏军队分别开进朝鲜半岛南北，以北纬38度为基准形成三八线。
+- **苏联鼓动朝鲜南进**：1949年新中国宣布废除列强在华一切租界及特权，含苏联在东北的中长铁路及大连旅顺特权，苏联不甘心，鼓动朝鲜进攻韩国，希望以仁川或釜山替代旅顺、大连地位，继续在亚洲发挥影响力。
+- **战争爆发与各方称谓**：1950年6月北朝鲜军队率先越过三八线南进，朝鲜称“祖国统一解放战争”，中国称“抗美援朝”，韩国称“625事件”，美国及西方国家称“朝鲜战争”或“韩战”（台湾地区称谓）。
+- **战争初期进程**：朝鲜人民军从三八线一路打到洛东江环形防御圈（今大邱至釜山一带）；1950年9月15日美军仁川登陆成功，将朝鲜人民军分割包围、逐次歼灭，收复三八线以南韩国领土。
+- **联合国军组成**：美军以联合国军身份参战，共十六国共同出兵；联合国军总司令为麦克阿瑟，其试图扩大战果将整个北朝鲜并入囊中，招致中国强烈不满——朝鲜半岛对中国是“唇亡齿寒”状态。
+## 志愿军参战与主要战役
+- **出兵与首次交火**：1950年10月19日志愿军跨过鸭绿江，10月25日与韩国军队首次交火，11月5日第一次战役结束。
+- **第二、三次战役**：第二次战役含长津湖战役（近年国内影视作品宣传）；第三次战役越过三八线，占领汉城（今首尔）、仁川、水源等地，推进至三七线（北纬37度一带）。
+- **停战与边界形成**：第五次战役（最后一次大规模战役）后双方在三八线互有攻防，形成今日朝韩边境：西部中朝占领开城、延安半岛和望京半岛；东部美军占领襄阳和金刚山地区（金刚山现为韩国著名旅游景点）。
+- **停战协定**：1953年7月27日双方正式达成停战协定，延续至今；朝韩仅名义停战，未实现真正和平，三八线非军事区（DMZ）现为旅游景点。
+## 朝鲜战争的影响
+- **奠定中国强国地位**：美国再不敢小瞧中国；1967年越南战争时期，中国警告美国绝对不允许越过北纬十七度线（南越与北越边境线），否则中国必将出兵越南，美国未敢越线。
+- **美国称“被遗忘的战争”**：联合国军最后一任司令官马克·克拉克承认，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。
+- **朝韩两败俱伤**：朝鲜和韩国本是一脉相承的血肉同胞，却分裂成两个国家，三八线的悲剧延续至今。
+## 朝韩分裂原因与现状
+- **美苏各自建立缓冲区**：美国在半岛南部单独建立韩国，为保护日本免遭苏联及共产主义势力影响；苏联需要在亚洲建立卫星附属国，故扶植北朝鲜独立，奉行对苏马首是瞻的指示。
+- **统一计划落空**：最初设想像奥地利那样在不同占领区受降后举行普选、建立统一民选政府，但美苏关系急转直下，所扶植领导人各有心思，因意识形态不同最终建立两个国家——这也是朝鲜战争爆发的缘由。
+- **当前对峙状态**：美国因惧怕朝鲜背后的中国和俄罗斯（朝鲜战争时中国出动志愿军、苏联提供空军掩护和武器后勤支持），未主动进攻朝鲜；朝鲜金家担心贸然发动战争后江山被颠覆，也不敢轻举妄动。
+- **统一前景判断**：若朝韩统一，大概率是韩国兼并朝鲜（经济影响和综合实力占优），北方有充足优质兵源及核武器、导弹等尖端武器；统一后对整个东北亚地区都是不稳定因素——参照越南统一第二年即进攻柬埔寨和泰国，被中国1979年出兵自卫反击。
+## 韩国军队战斗力评价
+- **1952年前战斗力弱**：战争初期韩军瞎指挥，差点被朝鲜团灭；1950年6月25日战争爆发后，7月10日起南部地面战斗主要由美军与朝鲜人民军进行，韩军只负责“冲人头”。
+- **拖累美军战线**：志愿军与美军占不到便宜时都从韩军战线突击，美军每次兵败都由韩军战线崩溃引起；第五次战役中志愿军从半岛东部反包围突击，打崩韩军前线，美国在韩国领土上撤销了韩国第三军团。
+- **1952年后形成战斗力**：美国重新整军训练备战后，韩军才形成基本战斗力；军官主体是二战时期日本人扶植的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁强征的农村青年。
+- **军队传统延续至今**：韩军一直贯彻二战时期昭和日军的武士道精神管理体制，关西兵、老兵欺负新兵，军队霸凌事件蔓延至今，是旧日军部队的一种延伸。
+## 抗美援朝而非收复台湾的决策原因
+- **海军实力不足**：台湾与大陆间海峡约100公里，中共刚建国没有相应海军实力，无法进行解放台湾的战斗。
+- **美国介入台海**：1950年朝鲜战争爆发后，美国参众两院视其为共产主义世界对自由世界的全面进攻，将台湾和韩国共同纳入亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。
+- **唇亡齿寒的战略考量**：美军越过三八线向朝鲜及中朝边境进发，触动中国敏感神经，“唇亡齿寒”深入人心；即便不愿与美国爆发全面战争，也不得不打——既然海上无法战斗，就发挥解放军陆军优势在陆地战斗。
+- **战斗意志的体现**：长津湖和上甘岭两场战役接连让美军惨败，至今是美国人挥之不去的梦魇。
+# 金句总结
+&gt; “美国再也不敢小瞧我们了。”
+- 背景：回答朝鲜战争对中国国际地位的影响时，指出战争奠定了中国强国地位，并导致美国在越南战争中未敢越过北纬十七度线。
+&gt; “他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。”
+- 背景：引用联合国军最后一任司令官马克·克拉克的自我承认，说明美国将朝鲜战争称为“被遗忘的战争”。
+&gt; “伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家。”
+- 背景：评价朝鲜战争对朝韩双方的深远伤害，指出三八线悲剧延续至今。
+&gt; “唇亡齿寒这么一个概念，就是深入人心。”
+- 背景：解释中国决定出兵抗美援朝的战略考量，因美军越过三八线进犯中朝边境，触动中国敏感神经。
+&gt; “既然海上没办法进行战斗，那就只能在陆地上进行战斗。”
+- 背景：回答为何选择抗美援朝而非收复台湾时，指出解放军陆军强大，故在陆地战场争取战略主动。
+&gt; “在长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。”
+- 背景：说明中国志愿军的战斗意志与战果，作为抗美援朝决策正确性的例证。
+&gt; “俄罗斯和朝鲜都不希望咱们过分强大，然后不想过多依附于我们，所以说在那个图们江出海口给封死了。”
+- 背景：解释图们江出海口问题长期未解决的原因，指出俄朝建桥封死航道、阻碍中国大船通行。
+&gt; “他就是一支充满着昭和军国主义时期那种思想余孽的，就是旧日军部队的一种延伸。”
+- 背景：评价韩国军队的体制传统，指出其以二战日军扶植的伪军为骨干，霸凌事件延续至今。
+# Q&amp;A 环节
+**发言人4**：这场战争开始和结束时，韩国和朝鲜的势力有很大差别吗？战争的改变大吗？
+**主讲人**：从中国角度来说，奠定了强国地位，美国再不敢小瞧我们，导致1967年越南战争时期中国警告美国不得越过北纬十七度线，美国未敢越线。这场战争在美国被称为“被遗忘的战争”，最后一任司令官马克·克拉克承认是美国历史上第一次在未取得胜利的情况下签署停战协议。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
+**发言人2**：现在越南还分南北吗？
+**主讲人**：没有，越南是统一的。美国最终放弃了南越，北越趁机会把南越统一了。
+**发言人2**：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
+**主讲人**：当然是韩国更好玩。朝鲜旅游限制严格，入境搜手机检查，没有无线网，只有平壤有自己的网络运营商，类似中国八九十年代状态，手机落后，国际漫游和网络非常贵。参观内容主要是主体思想和社会主义辉煌建设成就，类似文革时期那种思想，活在异次元世界当中。
+**发言人4**：他们普通人可以上网吗？
+**主讲人**：普通人不能上网，局域网都很有限，普通人连电脑和5G手机都用不起。因为外部有韩国用韩剧作为意识形态宣传武器，老百姓知道真相后会颠覆政权，所以才有那么多朝鲜老百姓往韩国跑，即脱北者。
+**发言人3**：他们有拿飞机往朝鲜发传单或韩国文化图片吗？
+**主讲人**：有的。朝鲜严防此类物品，只要被发现谁家私藏，肯定要追究连带责任。
+**发言人2**：朝鲜那边有啥好玩的？
+**主讲人**：也就平壤看看志愿军抗美援朝功绩，还有开城——朝鲜半岛三千年古都，特产小人参。
+**发言人3**：朝鲜有他们古代的文化吗？比如高丽，还有韩剧里讲的朝鲜古代将军什么的。
+**主讲人**：朝鲜半岛文明是中华文明的衍生物，有3500年历史，最早是商周时期形成初步文明，一直是中华文化圈的中原附属国，直到甲午战争清朝战败后朝鲜才脱离与中国的关系，成立大韩帝国，后来与日本合并，二战后复国又被分裂。
+**发言人6**：朝鲜是不是和北京或俄罗斯有一个很大的广场？平壤的金日成广场，是以领导人命名的吗？
+**主讲人**：对，以领导人命名，他们的大将军、大元帅这样的。
+**发言人4**：南北之间的割裂有什么历史渊源？为什么会成为两个政权？
+**主讲人**：一开始美国和苏联都希望在朝鲜半岛建立缓冲区。美国分出三八线以南单独建立韩国，是为保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建立卫星附属国，所以在朝鲜北部宣布独立。最初设想是像奥地利那样形成普选、建立统一民选政府，但美苏关系恶化极快，所扶植的领导人各有心思，因意识形态不同最终建立两个国家，这也是朝鲜战争爆发的缘由。
+**发言人4**：当时美国没有打败朝鲜，你觉得现在美国对朝鲜的态度是怎样的？
+**主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争时朝鲜快被美国完全占领，中国出动志愿军帮朝鲜把美国打回去，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南。美国忌惮这一因素，所以没有主动进攻朝鲜，也没再挑起半岛武装冲突。朝鲜金家也担心贸然发动战争后江山被颠覆，所以也不敢发动战争。
+**发言人7**：现在的朝韩对立局面可以认为是微妙平衡吗？如果当时没有冷战布局争夺半岛控制权，大一统的朝鲜半岛会是什么形态？
+**主讲人**：如果当时美国没有下场救援韩国，今日朝鲜可能会是苏联卫星国，用来牵制中国，也是威胁美国在亚洲尤其是日本的定时炸弹。现在朝韩若统一，大概率是韩国兼并朝鲜，毕竟经济影响和综合实力摆在那儿，北方有充足优质兵源及核武器和导弹等尖端武器，统一后对整个东北亚地区都是不稳定定时炸弹。当年越南统一后第二年就进攻柬埔寨和泰国，被逼到1979年中国出兵对越南发动自卫反击战，越南尚且如此，朝鲜半岛统一后局势更加不可控。
+**发言人3**：你感觉现在中国、俄罗斯和朝鲜之间关系怎么样？
+**主讲人**：各怀鬼胎。中国和朝鲜、俄罗斯的问题主要是图们江出海口问题，到今天还拖着没着落。
+**发言人4**：什么出海口？
+**主讲人**：图们江是俄罗斯和朝鲜的界江，是日本海的出海口。中朝俄边境那块国际水域航道可以通行，但俄罗斯和朝鲜建了一座小桥，大船没法过去。俄罗斯和朝鲜都不希望中国过分强大，不想过多依附于我们，所以把图们江出海口封死了。
+**发言人6**：朝鲜战争中朝鲜军队和韩国军队有没有发挥作用？
+**主讲人**：一开始韩国军队瞎指挥，差点被朝鲜团灭。6月25日战争爆发，7月10日以后朝鲜南部地面战斗主要是美军和朝鲜人民军进行，韩军一开始是冲人头角色。1952年之后美国把韩国重新整军训练，韩军才形成基本战斗力。此前韩军对美军像猪队友，志愿军跟美军占不到便宜时都从韩国军队战线突击，美军每次兵败都是韩国军队战线崩溃引起。第五次战役中志愿军从朝鲜半岛东部形成反包围突击，把整个韩国军队前线打崩，美国把韩国第三军团全部撤销。1952年前韩军战斗力不敢恭维，1952年后不可小视。韩军军官主体是二战时日本人扶植的伪军和傀儡部队骨干，士兵类似国民党抓壮丁形式强征农村青年，一直贯彻昭和日军武士道精神管理体制，老兵欺负新兵，军队霸凌事件蔓延至今。
+**发言人5**：1950年援朝时中国刚成立，实力不强，为什么选择抗美援朝而不是收复台湾？
+**主讲人**：台湾和大陆之间海峡距离约100公里，中共刚建国没有相应海军实力。1950年朝鲜战争爆发，美国参众两院普遍认为是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。解放军建军时没有海军实力，无法进行解放台湾战斗。但美军越过三八线向中朝边境进发，触动敏感神经，唇亡齿寒概念深入人心，即便不愿与美国爆发全面战争又不得不打。台湾的事已让中国很被动，朝鲜半岛要争取战略主动，解放军陆军很强，海上没办法战斗就在陆地战斗。长津湖和上甘岭接连让美军惨败，这两场战役到今天仍是美国人挥之不去的梦魇。</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7464/5645</t>
         </is>
       </c>
     </row>
@@ -14378,6 +15773,54 @@
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>对话记录</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t># 对话概况
+本次闲聊由发言人1发起“出门必带的三样东西”问题，五位发言人围绕个人随身物品及生活习惯展开漫谈。话题从必带物品（手机、充电宝、指甲刀、钥匙、皮圈、耳机、工卡等）自然延伸到电子锁替代钥匙、头发打理与形象偏好、胡子打理经历，再转到下雨与居住安全。以分享为主，未形成明确结论；差异主要体现在习惯层面，如发言人2因使用电子锁多年而“没有钥匙概念”，用指甲刀平替钥匙，而发言人1坚持必须带钥匙；发言人2上班必带刮胡刀（平均每三天一次，因胡子一天长几毫米），发言人5则每天带手机、耳机和工卡。值得记的锚点包括：发言人2留胡子时曾被误认为新疆少数民族；发言人3提到每年下雨园区门口积水、李博家曾被淹，发言人2据此建议住三楼以上。
+# 交流内容
+- **出门必带物品**：发言人1起头问出门必带三样东西，发言人2答`手机`、`充电宝`、`指甲刀`，并解释指甲刀可刮指甲、磨手掌；发言人3说`钥匙`，发言人1认同并称必须带钥匙。
+  - 发言人2称已用`电子锁`多年、没有钥匙概念，用指甲刀平替钥匙；还提到以前`扣耳勺`也挂钥匙上。
+  - 发言人4指出钥匙破坏性强、需套起来或挂起来，并说自己一定带`皮圈`绑头发；发言人2追问不带皮圈会怎样，发言人4答头发想绑时没法绑。
+  - 发言人5称每天带`手机`、`耳机`、`工卡`；发言人2说耳机和工卡都放单位，刷脸进门；发言人1说打卡用手机即可，但领`夜宵`需工卡。
+  - 发言人1称上班几乎只带手机，出差不带`手机卡`；发言人3补充出门带`纸巾`、下雨带`伞`。
+- **头发打理与形象**：发言人2好奇初中男生为何薅女生头发圈，发言人1表示没有此爱好；发言人2假设自己是女生会披发不绑，因绑发显得脑袋大。
+  - 发言人1认为散头发比绑着好看，不想让女生绑；发言人3建议弄个`公分`两边补点点。
+  - 发言人2提到高中时想留长发和胡子，后因不好打理放弃；留胡子时去学校报到曾被误认为`新疆少数民族`。
+- **下雨与居住安全**：发言人1说秋天容易下雨，发言人2好奇为何不是春天，发言人4认为`北京`夏天易下雨；发言人1称北京下雨少、无季节性。
+  - 发言人3提到每年下雨`园区门口`都是水，`李博`家曾被淹；发言人2建议住`三楼以上`，发言人3说李博家地势低。
+# 关键原话
+&gt; “手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。”
+- 背景：发言人2回答发言人1提出的“出门必带的三样东西是什么”问题。
+&gt; “对呀，我必须带钥匙，不带钥匙就行。”
+- 背景：发言人1回应发言人3说“钥匙”，表示自己出门必带钥匙。
+&gt; “钥匙哈。我我已经好多年的电子锁了，我都没什么钥匙的概念了都。然后所以说拿指甲刀来平替钥匙了。”
+- 背景：发言人2回应发言人1必须带钥匙的说法，说明自己用电子锁多年、以指甲刀替代钥匙。
+&gt; “我一定会带一个那个皮圈就绑头发的。”
+- 背景：发言人4在讨论出门必带物品时补充自己必带绑头发的皮圈。
+&gt; “对，所以说我上班必带三件套，充电宝、手机、刮胡刀。”
+- 背景：发言人2在讨论上班必带物品时总结自己的三件套。
+&gt; “我现在每天就是手机、耳机和工卡。”
+- 背景：发言人5回应“没人上班带耳机吗”，说明自己每天必带手机、耳机和工卡。
+&gt; “就他那个地势吧，然后就是家里，然后他那个地势。”
+- 背景：发言人3回应发言人2询问李博家被淹是否因住一楼，说明是地势原因。
+# 共识与分歧
+**共识与分歧**
+- **共识**：大家普遍认同出门必带物品以实用、必需为原则，且多数人依赖手机作为核心工具（如打卡、门禁），反映出电子化替代实体物品的普遍趋势。此外，对长头发打理不便、留胡子难打理等体验有一致感受，因此多数人倾向简洁、易打理的形象。
+- **分歧**：在出门必带物品上存在习惯差异——有人坚持带钥匙（发言人1、3），有人因使用电子锁多年而完全无钥匙概念（发言人2）；有人必带刮胡刀（因胡子长得快、不带会痒），有人则不带。在头发打理上属审美差异——发言人1认为散头发更好看，发言人2假设自己是女生会选择披发显脸小，而发言人4提到皮圈是必带品。关于下雨季节属认知差异——发言人1认为秋天易下雨，发言人4认为北京夏天易下雨，发言人3则提到园区门口每年下雨积水。
+- **倾向**：本场以分享个人习惯为主，未形成明确结论；多数发言围绕个人便利与舒适展开，分歧性质多为**习惯差异与审美差异**，而非价值取舍。
+# 延伸话题与后续
+- **秋天与春天哪个季节更容易下雨**：发言人1提出“秋天容易下雨”，发言人2好奇为何不是通常认为的春天，发言人4认为北京夏天易下雨，发言人1补充北京下雨少且无季节性，讨论未形成定论。
+- **李博家被淹的后续**：发言人3提到每年下雨园区门口都积水，李博家曾因地势低被淹，发言人2据此建议住三楼以上，未再深入。</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3851/2050</t>
         </is>
       </c>
     </row>
@@ -14571,6 +16014,46 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为一次围绕手机常用APP及音乐、视频使用习惯的漫谈式交流，五位发言人（发言人1至发言人5）参与。讨论由发言人1发起「手机里最常用的三个APP」话题，随后自然延伸至AI助手、视频平台、音乐应用及歌手偏好等议题。议题范围包括：常用APP列举、AI助手（小布、豆包、百度千问等）的使用体验与准确性疑虑、视频播放器（腾讯视频、爱奇艺、优酷、芒果TV、B站）的广告与VIP问题、音乐APP（网易云、酷狗、酷我、虾扎、苹果音乐）及单框架手机适配问题、歌手与乐队偏好（Taylor Swift、谢霆锋、五月天、周杰伦等）及Taylor Swift重新走红的原因。讨论以分享观点为主，未形成统一结论；整体呈漫谈发散式推进，由APP话题逐块延伸至音乐与歌手讨论，期间穿插对AI准确性的质疑、单框架手机无法下载YouTube及网易云不适配等具体问题。
+# 发言要点
+## 常用APP与AI助手使用
+- **发言人2**：常用知乎、小红书、谷歌；对AI回答准确性存疑，仍停留在浏览器、纸质地图、尺子圆规铅笔标注的思维模式，自比「大家在用GPS，我还在用纸质地图」。
+- **发言人3**：常用微信、抖音、淘宝、京东；认为AI小助手比浏览器更全面、回答更精准、总结性强，自己也下载了豆包。
+- **发言人4**：常用微信、小红书；现在不用浏览器，直接搜手机自带的小布AI助手。
+- **发言人5**：常用B站、YouTube，希望AI能识别中英混杂表达；指出单框架手机现在连YouTube都下不了。
+- **发言人1**：手机里装有百度千问、吉米等多个AI应用；反问「你能判断他说的是对的吗」，对AI回答可靠性提出质疑。
+## 视频与音乐APP讨论
+- **发言人3**：常用腾讯视频、爱奇艺、优酷、芒果TV等播放器；提到现在很多电视剧可看广告换取VIP时长。
+- **发言人2**：因广告时间太长「耗不起」，直接用B站观看；以前常用酷狗、酷我，现提及国外音乐平台虾扎，称其欧美演唱会版本比国内网易云更多。
+- **发言人1**：认为虾扎上多是小众歌手，大牌因版权纠纷播不出来。
+- **发言人5**：常用网易云音乐，但单框架手机网易云一直不适配，现用卓翼通替代。
+- **发言人4**：通勤路上听音乐，需用降噪耳机；发言人2补充在柏林坐地铁时因地铁安静，听音乐代入感强。
+## 歌手与乐队偏好
+- **发言人3**：因刷到谢霆锋演Taylor Swift而喜欢谢霆锋，提及《玉蝴蝶》等九十年代作品。
+- **发言人1**：认为五月天早期作品好，新发的还行但「唱不上去了」。
+- **发言人2**：疑惑Taylor Swift为何重新火起来——中学时期（2010年代开头）她已很火，后因绯闻消沉，但对九零后和零零后影响都很深；提及《Speak Now》《Back To December》《Love Story》等歌，并回忆其与猫头鹰之城主唱亚当·杨的绯闻，称当时从东南卫视台湾节目看到。
+- **发言人4**：对Taylor Swift绯闻「没有很关注」，但承认其全球影响力。
+# 共识形成
+- **一致意见**：与会者普遍认可AI助手在回答全面性、精准度与总结性上优于传统浏览器搜索，发言人3明确表示「AI这个小助手更全面一点，回答的更精准一点，然后总结性比较强」；同时多人（发言人1、3、4、5）已实际使用豆包、小布、百度千问等AI应用，反映从浏览器向AI助手迁移的**共同使用趋势**。
+- **主要分歧点**：发言人2与其余成员在AI工具信任度上不一致——发言人2明确表示「不太确定它是否说的是对的」，仍停留在浏览器、纸质地图、尺子铅笔标注的思维模式，自比「大家在用GPS，我还在用纸质地图加尺子、圆规和铅笔标注」；其余成员未对此提出反驳或说服，分歧未获解决。
+- **倾向性认识**：在视频观看上，发言人2因广告时间过长不愿等待而倾向直接用B站观看，发言人3提及可通过看广告换取VIP时长，但发言人5指出「APP太多了，都不知道开哪个」，反映对多平台付费与广告模式的普遍不满；在音乐平台内容上，发言人2认为国外平台虾扎（Spotify）的欧美演唱会版本更多，发言人1则指出该平台「唱的都是一些小众歌手」，大牌因版权纠纷播不出来，双方对平台内容优势判断不一致。
+# 待探讨问题与后续
+- **未确认**：AI 助手回答的准确性是否可靠，发言人2对 AI 回答持怀疑态度，仍偏好浏览器、纸质地图、尺子铅笔标注的思维模式，与会者未就此达成共识。
+- **待核实**：单框架手机无法下载 YouTube、网易云音乐不适配的具体原因，发言人5指出需用卓翼通替代，但原因未明确。
+- **未定论**：Taylor Swift 重新火起来的原因，发言人2疑惑其为何在消沉后再度走红，与会者未给出明确解答。</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4259/2011</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="13.5" customHeight="1" s="9">
       <c r="A47" s="6" t="inlineStr">
@@ -14742,6 +16225,70 @@
           <t>专题讲座</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次讨论由主持人发起，围绕2022年俄乌战争中俄军的实际表现展开，对比游戏与历史中的“钢铁洪流”印象，探讨俄军表现是否为其真实状态。讨论面向对军事、地缘政治及俄罗斯文化感兴趣的参与者，以自由交流形式进行。内容覆盖四个板块：俄军在俄乌战争中的表现与真实状态、游戏与媒体中的俄军形象、俄罗斯的地缘认知与欧洲态度、俄罗斯旅游与文化印象。核心判断包括：俄军单兵素质强但总体拉垮，主要短板在后勤和指挥；俄军主动进攻表现差，但防守反击时能迸发战斗力；欧洲将乌克兰视为“欧洲之门”，因俄罗斯被蒙古统治二百年而视其为亚洲蛮族，故全力支持乌克兰。讨论锚点包括2022年基辅攻防战、2014年克里米亚事件及《红警》等游戏形象。对听众而言，有助于理解俄乌冲突背后的军事现实与地缘逻辑，破除游戏与媒体塑造的刻板印象。
+# 核心观点与论证
+## 俄军单兵强而整体拉垮
+- **单兵素质与整体反差**：发言人1认为俄军单兵素质很厉害，但总体很拉垮，主要问题在后勤和指挥上，形容为「矮脚巨人」——像柯基一样腿短撑不起庞大身躯。
+- **主动进攻与防守反击反差**：发言人4认为俄军主动进攻时表现差，但被打到家破国亡时能迸发战斗力，擅长打防守反击。
+- **战场形态退化**：发言人1指出双方重装备耗光后，俄乌战场从钢铁洪流变成隔着战壕互相扔手雷、用无人机互炸的「菜鸡互啄」状态；发言人4评价俄乌战场与二战相比没多大进步，只是多了无人机。
+- **腐败侵蚀战力**：发言人3提到俄军腐败问题，如国防部长「特别会盖房子」；发言人1补充情报官员将用于策反乌克兰官员的经费全部贪污瓜分，导致乌克兰高官未收到策反经费。
+## 俄军战前误判与情报失灵
+- **基层官兵不知开战**：发言人1称俄军基层官兵不知道2022年会进攻乌克兰，许多部队收到命令以为是去演习，结果演着演着就进入乌克兰。
+- **遭遇民兵自发抵抗**：第一批进入乌克兰的俄军遭遇的是民兵自发抵抗，而非军队有组织的进攻，一来二去从闪电战变成持久战。
+- **普京信息茧房误判**：发言人1认为普京飘了、活在自己的信息茧房里，对乌克兰抵抗意志与自身情报系统失灵缺乏准确判断。
+- **克里米亚埋下仇恨**：2014年俄罗斯占领克里米亚后，乌克兰上下迸发民族仇恨，发言人1类比为类似九一八事变的耻辱感——一枪不发丢掉整个克里米亚，民众对当权者无能腐败非常不满。
+## 游戏中的俄军形象与现实脱节
+- **游戏形象360度反转**：发言人1指出《战地风云》《使命召唤》《红警》等游戏中俄军或苏军形象与现实俄军表现有360度的改变。
+- **西方主导的抹黑**：发言人2认为《红警》是美国为黑苏联而制作；发言人4补充西方主导的游戏将苏联形象描绘成反面、暴力、研究邪乎武器、规模夸张的形象。
+- **思想被污名化**：发言人1举例心灵控制器，认为共产主义解放世界的思想被抹黑成心灵控制器，把毛子形容成暴力美学的形象代言。
+## 欧洲将俄罗斯视为亚洲蛮族
+- **欧洲之门与欧亚分界**：发言人1指出乌克兰在欧洲认知中被称为「欧洲之门」，欧洲人认为欧亚分界线在乌克兰而非乌拉尔山脉——白俄罗斯多为沼泽地，缺乏大规模运输通道走廊。
+- **蒙古统治的历史隔阂**：俄罗斯人被蒙古人统治二百年，不被欧洲认可接纳，被视为长着欧洲面孔的亚洲游牧民族；发言人4补充古代中国也视北方为蛮族。
+- **欧洲支援乌克兰的动因**：欧洲自发达乌克兰、武装并守住乌克兰，要把俄罗斯挡在亚洲之外；若俄罗斯握紧乌克兰，欧洲会再次生活在曾经的阴影之下。
+- **俄罗斯必须控制乌克兰**：发言人1认为俄罗斯立国靠乌克兰为立国资本，没有乌克兰的俄罗斯帝国终究沦为边缘亚洲国家，不被欧洲待见。
+## 俄罗斯文化底蕴与藏品掠夺
+- **东宫艺术宝库**：发言人1推荐圣彼得堡东宫，称其为世界四大艺术博物馆之一，连续去三次、分不同区域仍未逛完馆藏珍宝。
+- **藏品来源多元**：东宫藏品包括列强殖民掠夺、王室联姻赠送、二战打进德国后运回的纳粹藏品；往东有朝鲜半岛、蒙古、西藏、西夏王陵、敦煌的产品，往南有中东、阿富汗、中亚、埃及、北非、奥斯曼土耳其时期的藏品。
+- **掠夺方式与英法不同**：发言人1指出俄罗斯未像英法那样圆明园式掠夺，多以探险队名义获取，中亚斯坦国曾是俄国属地，如乌兹别克斯坦塔什干是一带一路丝绸之路走廊的重要文明之都。
+# 金句总结
+&gt; “俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上。”
+- 背景：总结俄军在俄乌战争中的整体表现，指出单兵能力强但后勤与指挥是短板。
+&gt; “从一种钢铁洪流变成了最后的菜鸡互啄。”
+- 背景：描述俄乌双方重装备耗光后，战场沦为战壕扔手雷与无人机互炸的消耗战状态。
+&gt; “普京飘了，他活在他自己的一个信息茧房里边。”
+- 背景：分析俄军开战准备不足的根源，指情报官员贪污策反经费、普京误判形势。
+&gt; “乌克兰上下迸发出了一种民族间的一种仇恨，就会在我们看来就有一种类似于像九一八事变的一种耻辱。”
+- 背景：解释2014年克里米亚被占后乌克兰的抵抗意志来源，类比九一八事变带来的民族屈辱感。
+&gt; “没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。”
+- 背景：论证俄罗斯必须控制乌克兰的地缘逻辑，否则将被欧洲视为亚洲边缘国家。
+&gt; “在欧洲人的认知里面，欧亚分界线在乌克兰那边。”
+- 背景：说明欧洲将乌克兰视为欧洲之门、将俄罗斯挡在亚洲之外的地缘认知依据。
+&gt; “终究就是被当成是亚洲游牧民族来看待，就是长着欧洲人面孔的亚洲游牧民族。”
+- 背景：解释俄罗斯因被蒙古统治二百年而不被欧洲接纳，被视为半兽人般的蛮族形象。
+&gt; “俄罗斯的无人机都是靠伊朗给他的。”
+- 背景：指出俄军在无人机装备上对伊朗的依赖，说明其军工补给的实际短板。
+# Q&amp;A 环节
+**发言人4**：俄罗斯打仗是不是得给它打到要家破国亡了，才能迸发出战斗力，打防守反击？主动进攻感觉就不太行。
+**发言人1**：可以这么说。俄军单兵素质很厉害，但总体拉垮，主要问题在后勤和指挥上，像矮脚巨人，腿短撑不起庞大的身子。加上情报官员把策反乌克兰官员的经费贪污瓜分了，基层官兵接到命令还以为是演习，结果进乌克兰遭遇的是民兵自发抵抗，从闪电战打成了持久战。
+**发言人4**：感觉俄乌战场打得跟二战时候没啥进步，多了点无人机，还是扔手雷，不太先进。
+**发言人1**：对，双方重装备都耗光了，只能隔着战壕互相扔手雷、用无人机互炸，从钢铁洪流变成了菜鸡互啄。俄罗斯的无人机还是靠伊朗给的，乌克兰则有北约持续输血，有点像越战的形式。
+**发言人2**：去俄罗斯旅游还行，但出俄罗斯之后办美签，他们会不会拒你？
+**发言人1**：会卡得挺严。我上次去美国，因为去过好几次俄罗斯，在边境入口就被拦下来问去俄罗斯干嘛，我瞎掰扯了一通，差点被怀疑是间谍。在美国人认知里咱们是普通国家，但在波兰、乌克兰、波罗的海三国这些东欧国家眼里，俄罗斯就是敌人、蛮子、半兽人。
+**发言人4**：俄罗斯地域那么宽阔，远东地区和欧洲那头差别大不大？
+**发言人1**：总的来说还是以俄罗斯族为主，他们也是像美国西进运动那样东扩，源源不断地淘金移民过去的。</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6103/2995</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="13.5" customHeight="1" s="9">
       <c r="A48" s="6" t="inlineStr">
@@ -14839,6 +16386,58 @@
           <t>专题讲座</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次讨论由发言人1主持，围绕电影《南京照相馆》的观影印象与历史背景展开，参与者包括发言人2、发言人3、发言人4、发言人5。讨论先由各人分享观影感受，随后发言人1系统介绍南京大屠杀的历史背景，并辨析电影中真实与虚构的细节，最后延伸至各地抗战纪念馆的参观体验与南京大屠杀的历史认知。核心判断包括：日军自九一八事变以来首次在淞沪抗战遭遇成规模抵抗，伤亡惨重，攻破南京后因军纪失控酿成大屠杀；电影主要人物为虚构，但照片拍摄、中华门城墙战斗、挹江门惨案及战犯审判等细节均有史实依据。讨论以1937年8月13日淞沪抗战、松井石根与朝香宫鸠彦亲王等专名为锚点。对听众而言，本次交流有助于厘清电影叙事与史实的边界，并增进对南京大屠杀历史背景的理解。
+# 核心观点与论证
+## 电影主要人物虚构、照片拍摄真实
+- **人物虚构**：电影中主角与日本军官建立友谊等主要人物关系为虚构，原文明确「电影里的主要的人物是虚构」。
+- **照片拍摄真实**：真实历史中由两名美国传教士拍摄日军暴行照片，而非电影所述方式。
+- **照片保存与提交**：一名负责为日军冲洗照片的中国后期人员无意发现日军拍摄的暴行照片（当时属日本禁文），偷偷拷贝藏匿，抗战后递交国民政府军事法庭，作为审判日本战犯的证据。
+## 南京大屠杀成因：日军军纪失控与指挥官更替
+- **淞沪抗战背景**：1937年8月13日国民党军队在上海与日军激战，因实力原因撤退，日军追击至南京；此前自九一八事变、七七事变后日军未遭遇成规模抵抗，淞沪抗战是首次迎头痛击，伤亡惨重。
+- **军纪约束缺失**：日军从上海打到南京历时约四个月，缺乏纪律与军纪约束，战场上「已经杀红眼」，处于战争下人性泯灭状态，攻破南京后发生惨无人道的南京大屠杀。
+- **指挥官更替**：原指挥官松井石根因生病被临时替换，他曾接连发布命令避免日军在上海至南京沿线烧杀抢掠，以免增强中国军民抵抗意志；接任者为裕仁亲王的叔叔朝香宫鸠彦亲王。
+- **朝香宫鸠彦亲王**：极度追随日本国内盛行的脱亚入欧思想，认为亚洲国家除日本外皆低贱；上任后发布第一道命令「不留俘虏」，导致日军对俘虏格杀勿论，后蔓延至平民群体，最终引发南京大屠杀。
+## 日军暴行心理根源
+- **应激创伤与侮辱感**：日军自九一八事变以来未遭像样大规模战争，淞沪抗战使其遭受「前所未有的侮辱」及战场应激创伤反应，结合日本自古以来攻破敌方城镇以屠城进行狂欢与麻痹的传统。
+- **高压武士道精神**：自上而下的高压武士道精神与欺凌霸凌背景之下，日军更想寻找宣泄口，抱着「兴许活不到战争结束，趁活着放纵自己」的心态。
+## 电影中真实历史细节
+- **中华门城墙战斗**：电影开头日军进攻南京时中华门城墙的战斗为真实历史细节。
+- **挹江门惨案**：军队与平民撤退时宪兵未让撤出，守挹江门部队未收到撤退命令，两方信息差导致最终惨案。
+- **战犯审判与枪决**：电影尾声审判中，打进南京的谷寿夫（第六师团师团长）等南京大屠杀主犯及基层日军军官被枪决，为真实历史。
+## 各地抗战纪念馆参观体验
+- **沈阳伪满洲国博物馆**：发言人2上午前往，下午已排不上队，整个广场全是人，必须预约。
+- **唐山大地震纪念馆**：发言人2参观时人数同样很多，认为国人对此类历史「蛮有同情心、蛮有爱心」。
+- **上海淞沪会战纪念馆**：发言人3参观时即使下大雨馆内也全是人，大人小孩都很多，认为上海宣传做得好，可能与党的诞生地有关。
+- **南京大屠杀纪念馆**：发言人3表示难抢票，发言人4多年前去过，当时还可以，馆内有各种实验类展品。
+# 金句总结
+&gt; “在战争底下就是那种人性的泯灭吧。”
+- 背景：解释日军攻破南京后发生大屠杀的原因，因长期战争与缺乏军纪约束导致人性丧失。
+&gt; “从他们当时那样的一个心态来说，就觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”
+- 背景：分析日军自九一八事变以来首次遭遇淞沪抗战的迎头痛击后，攻入南京时的心理动因。
+&gt; “因为从他自己的角度来说，就是说‘我兴许我活不到战争结束，那我就趁着我还活着的时候，我对自己进行一种放纵。’”
+- 背景：剖析日军结合屠城传统与高压武士道精神，以暴行作为宣泄与狂欢的心理机制。
+&gt; “在他的眼里，就是整个亚洲国家除了日本以外，其他国家都是低贱的。”
+- 背景：描述接任日军统帅的朝香宫鸠彦亲王所持脱亚入欧思想的极端立场。
+&gt; “果然他上任之后发布的第一道命令就是不留俘虏，月后祭坟。”
+- 背景：说明朝香宫鸠彦亲王接替生病的松井石根后，下达导致军纪失控、最终酿成南京大屠杀的命令。
+# Q&amp;A 环节
+**发言人4**：电影里主角和一名日本军官建立友谊，这个情节是虚构的还是真实的？
+**发言人1**：电影里的主要人物是虚构的，但照片的拍摄是真实的，只是不是以电影里描述的方式进行的。真实历史是当时两名美国传教士拍摄了日军暴行照片；同时期有一名负责给日本人冲洗照片的中国人，无意间发现这些在日本属于禁文的暴行照片，偷偷拷贝藏起来，抗战后递交给国民政府军事法庭，作为审判日本战犯的证据。
+**发言人5**：现在好多日本人还不承认南京大屠杀这件事。
+**发言人1**：对。电影里真实的历史细节包括：开头中华门城墙的战斗是真实的；挹江门撤退时，宪兵没让平民撤出去，守挹江门的部队没收到撤退命令，两边信息差导致最终惨案；电影尾声审判中，谷寿夫（第六师团师团长）等打进南京部队的主犯和上了新闻的基层日军军官被枪决，也是真实历史。</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4228/2306</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="13.5" customHeight="1" s="9">
       <c r="A49" s="6" t="inlineStr">
@@ -14920,6 +16519,52 @@
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议围绕日本国家概况展开探讨，由发言人1主导讲解、发言人2参与交流，共两人。讨论由发言人1发起，旨在了解大家对日本的印象与认知，话题涵盖日本文化的历史阶段与特征、民族性格与天皇制度、购物体验与中古店、旅游推荐等。整体以分享观点为主，未形成统一结论。讨论按议题逐块推进，从文化历史切入，延伸至社会制度、消费现象与旅行体验。原文涉及的关键锚点包括日本文化三次转折（大化改新、明治维新、和平宪法转型）、1945年二战后麦克阿瑟进驻日本、广场协议后泡沫经济崩溃催生中古店产业。
+# 发言要点
+## 日本文化的历史阶段与特征
+- **发言人1**：日本文化没有原创，属外来接收后的本土化转型，在吴越文化基础上进行改造，经历三次转折——古代大化改新时期、近代明治维新时期、二战后和平宪法转型时期。
+- **发言人1**：大化改新后日本大规模向中国和朝鲜半岛学习，在和服、制茶、漆器等传统印象上完成本土化转型。
+- **发言人1**：明治维新后日本积极向欧美列强看齐，将英国和德国的法度利器学入其中。
+- **发言人1**：二战后美国为日本制定和平宪法，社会结构大规模转型，同时期积极向美国看齐，形成动漫、二次元、汽车工业、铁道工业等今日印象。
+- **发言人2**：喜欢日本文化，读研时上过讲日本文化的课，涉及漆艺、茶艺等传统文化；读过老舍《四世同堂》后，觉得民族仇恨还是应该有一点影响。
+- **发言人1**：追问发言人2所指日本文化具体是哪个历史阶段，因日本文化无原创、均为外来接收后本土化改进。
+## 日本民族性格与天皇制度
+- **发言人2**：日本是岛国、气候不稳定，发展农业可能遭遇海啸等灾害，因此民族性格容易极端。
+- **发言人1**：古代天皇对各地封建君主而言是吉祥物般的存在，类似东汉末年或战国时期的天子，不能退位，被当作神灵供奉，以精神层面控制老百姓。
+- **发言人1**：1945年二战结束后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，从精神上打破固有认知，推动社会转型。
+- **发言人1**：现在天皇是象征性存在，类似英国和西班牙的君主立宪制，天皇及皇室成员不能参与政治，政治由国会和内阁选出首相执政。
+- **发言人1**：美国在二战后把日本改造成英美海洋法系国家结构；天皇没有实权，靠政府养着，存在感不如英国国王——英国国王还是整个英联邦国家的名义元首，日本只有本州岛范围。
+- **发言人1**：除日本、英国外，西班牙也有皇室，泰国也有皇室；教皇属宗教领域而非国家体制，体制上与日本较相近的是英国和西班牙。
+## 日本购物体验与中古店
+- **发言人1**：秋叶原是动漫周边发行地，数码宝贝玩偶、铁甲小宝原装及数码宝贝第二部黑暗战路暴龙兽合金版都是秋叶原最早发行。
+- **发言人1**：日本奢侈品便宜，中古店（二手奢侈品商店）很多；广场协议后日本泡沫经济一夜崩溃，失业上班族将高档大衣、西装、皮具、皮鞋等通过二手回收寄卖，催生中古店产业。
+- **发言人1**：中古店在上海有很多，能买到LV、Burberry、古奇等上个世纪知名大牌；男性款式相对少，范围有限。
+- **发言人2**：去日本购物会买化妆品、美妆、护肤品。
+- **发言人1**：法国、意大利、韩国也是女性购物热门地，买化妆品；男性买名牌、化妆品、巧克力，白色恋人巧克力是常见选择。
+## 日本旅游推荐
+- **发言人1**：推荐东京、大阪、镰仓、京都、名古屋等城市；东京有很多美食、购物、博物馆。
+- **发言人1**：去日本最喜欢爬山，爬富士山、看古城、逛博物馆；镰仓气候夏天比较舒服。
+# 共识形成
+- **一致意见**：日本文化在吴越文化基础上进行本土化转型，经历大化改新、明治维新、和平宪法转型三次转折，分别向中国与朝鲜半岛、欧美列强、美国学习；天皇现为象征性存在，不能参与政治，政治由国会和内阁选出首相执政，日本被改造成英美海洋法系国家结构。
+- **倾向性认识**：发言人2认为日本岛国气候不稳定，民族性格容易极端；发言人1补充古代天皇对各地封建君主是吉祥物般的存在，类似东汉末年或战国时期的天子，二战后麦克阿瑟要求天皇公开露面以打破其神格。
+- **分歧点**：发言人2询问日本民众现在对天皇是否还有崇拜，发言人1回应称已无崇拜，类似英国和西班牙的君主立宪制，天皇靠政府养着、无实权；但发言人2未明确接受此判断，仅以提问形式表达疑虑。
+# 待探讨问题与后续
+- **未确认**：日本民众现在对天皇是否仍有崇拜，发言人2提出此疑问，发言人1回应称天皇已无实权、为象征性存在，但未对民众情感层面作进一步核实。
+- **待核实**：二次元的英文表达方式，发言人1在讨论中提出此问题，现场未给出明确答案。
+- **未定论**：日本文化具体指哪个历史阶段，发言人2提及喜欢日本传统文化（漆艺、茶艺）与现代文化艺术，发言人1追问具体时期，讨论未形成明确界定。</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>4892/2069</t>
         </is>
       </c>
     </row>
@@ -15129,6 +16774,65 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为文学话题的延伸讨论，共5位发言人参与，围绕《三国演义》与《红楼梦》两部经典展开自由交流。三国部分由发言人1发起，从成员对三国的整体印象切入，依次谈及赤壁之战的深刻印象、阵营偏好（发言人2倾向蜀汉刘备阵营）、刘备称汉中王引发的连锁反应（吕蒙白衣渡江、夷陵惨败）、借荆州与湘水划界、单刀赴会的历史原型、白衣渡江的道德评价、东吴大都督周瑜、鲁肃、吕蒙、陆逊的结局，以及魏延烧栈道行为与谋反的界限、三顾茅庐与隆中对战略及其在失去荆州后的失效。红楼梦部分由发言人4提出多种解读角度，讨论涉及前八十回与后四十回的作者问题、高鹗续本的合理性、第五回判词对结局的预示、林黛玉与薛宝钗的人物性格变化、晴雯与袭人的人物映射，以及林黛玉代表明朝、薛宝钗代表清朝等索隐式解读。整体以分享观点为主，未形成统一结论；讨论按三国、红楼梦两大议题逐块推进，三国部分由发言人1主导史实补充，红楼梦部分由发言人4、发言人2、发言人3交替发言，发言人间有简短互动与追问。
+# 发言要点
+## 三国印象与历史细节讨论
+- **发言人2**：三国到诸葛亮去世就基本差不多了，后面没看完，不知道讲啥了，认为后续内容没意思。
+- **发言人1**：补充正史后续——姜维北伐、孙权二宫之争（晚年昏庸害死两子致东吴朝廷大乱）、邓艾偷渡阴平、姜维反间计自爆、刘禅投降、西晋灭吴。
+- **发言人2**：印象最深刻的是赤壁，认为三国前面比后面有意思。
+- **发言人2**：受《三国演义》影响偏好蜀汉刘备阵营，认为刘备白手起家。
+- **发言人1**：刘备若未称汉中王，孙权可能不会彻底决裂；称王引发连锁反应——吕蒙白衣渡江、刘备伐吴失败（夷陵惨败）。
+- **发言人1**：讲述借荆州细节——孙权只要求交还部分地区，刘备不乐意，孙权派兵夺荆南三郡；曹操攻汉中后刘备回师，双方签湘水划界（湘水之盟）。
+- **发言人1**：单刀赴会实为鲁肃与关羽各带随从在中立区谈判，被罗贯中美化为关云长只身赴险。
+- **发言人1**：刘备不还荆州把孙刘联盟信任搞没；孙权打合肥不下，索性偷荆州袭关羽。
+- **发言人2**：白衣渡江伪装成商人，突破底线、口碑不好，开了坏头。
+- **发言人1**：吕蒙白衣渡江偷盟友家，后世把「小偷鼠辈」与吕蒙名字划等号。
+- **发言人1**：东吴大都督结局——周瑜正史被射毒箭阵亡，鲁肃得瘟疫病故，吕蒙病故，陆逊在二宫之争时被孙权活活逼死（因问责孙权立太子后让两子争斗）。
+- **发言人2**：东吴后期政治斗争严重、内斗狠，几个大都督都没好下场。
+- **发言人1**：刘禅自知能力不行完全放权诸葛亮；诸葛亮去世后姜维无力回天，刘禅轻信黄皓谗言，姜维是魏国降将、无说服力，众人不服。
+- **发言人1**：魏延正史无谋反之心，只是不甘心大军撤退，烧了悬崖边栈道；若非姜维断后挡住司马懿军队，后果不堪设想——行为与谋反无异，根源是与杨仪个人矛盾上升至军队层面。
+- **发言人5**：讲述三顾茅庐——刘备中原屡战屡败、深感缺乏谋士，经推荐得知诸葛亮有卧龙之才，携关羽张飞三次拜访（第一次诸葛亮外出、第二次逢风雪、第三次终见），诸葛亮被打动提出隆中对（联合孙权），同意辅佐刘备。
+- **发言人1**：隆中对核心是横跨荆益、外结好孙权、西和诸戎、趁魏国变动北伐；白衣渡江后蜀汉失荆州全境，横跨荆益不成立，与结好孙权直接矛盾。
+- **发言人1**：诸葛亮北伐目标转向关中平原和陇西（今陕西、甘肃南部），希望纵跨凉益以图中原；第一次北伐赢面大，因马谡兵败街亭而破产，后期只能拖延魏国灭蜀时间，诸葛亮与姜维北伐更像绝望中的抗争。
+## 红楼梦版本与人物讨论
+- **发言人4**：红楼梦有多种解读角度，女生可能当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在是没有解开的谜底。
+- **发言人3**：红楼梦只写了前八十回，后面是别人续写。
+- **发言人2**：提到有「反清复明」的版本解读，认为真正意义与当时朝代、社会有关。
+- **发言人4**：不知道只有前八十回时，读高鹗续的后四十回觉得挺合理；知道后反复读前八十回，发现林黛玉性格变了很多，贾母对林黛玉的态度也有变化。
+- **发言人3**：第五回贾宝玉梦游太虚幻境，判词已把结局交代了。
+- **发言人4**：判词没点明确——探春、史湘云结局都是猜的，最后谁和贾宝玉在一起也没说清。
+- **发言人5**：问悲剧原因——贾宝玉与林黛玉真心相爱却被迫娶薛宝钗。
+- **发言人4**：林黛玉死是后四十回内容、非原作所写，但原作意图肯定是悲剧。
+- **发言人4**：晴雯是林黛玉的替身（性格像林黛玉），袭人性格像薛宝钗；晴雯之死是曹雪芹原笔，映照后面情节。
+- **发言人2**：看到解读说林黛玉代表明朝、薛宝钗代表清朝。
+- **发言人4**：有人解读秦可卿是前朝公主；秦可卿是金陵十二钗正钗之一，可惜早逝。
+- **发言人4**：第五回贾宝玉在秦可卿床上睡觉做梦到太虚幻境，看到十二金钗正钗（小姐）与副钗（丫鬟）的判词，对应每个人命运。
+- **发言人2**：询问为何选高鹗后四十回作为官方结尾。
+- **发言人4**：高鹗版总体比较合理，官方说法是在残稿上梳理完善、未违背作者原意，但写作细节和诗词能力不及曹雪芹。
+- **发言人3**：北京植物园（北苑所）旁边村子有曹雪芹小道，之前爬山看到过。
+- **发言人4**：北京植物园里有曹雪芹的故居（工具）。
+# 共识形成
+- **一致意见**：三国部分，发言人2与发言人1均认为诸葛亮去世后三国故事基本接近尾声，后续内容吸引力不足；双方还一致认为吕蒙白衣渡江偷袭盟友突破底线、口碑不佳。红楼梦部分，发言人3、发言人4、发言人2一致确认《红楼梦》原著仅存前八十回，后四十回为高鹗续写；发言人4与发言人3均认可第五回判词已预示人物结局，但探春、史湘云等具体结局仍属猜测。
+- **倾向性认识**：发言人2受《三国演义》影响偏好蜀汉刘备阵营，认为刘备白手起家；发言人1则从正史角度指出刘备称汉中王引发吕蒙白衣渡江、夷陵惨败等连锁反应，双方对刘备评价侧重不同但未正面交锋。红楼梦部分，发言人4认为高鹗续本总体合理、未违背作者原意，发言人2对此未明确反对，仅就续本选择缘由提出疑问。
+- **主要分歧点**：关于魏延，发言人1主张其无谋反之心，但烧毁栈道的行为与谋反无异；发言人2仅提及魏延被斩，未展开评价。关于东吴大都督结局，发言人1详述周瑜、鲁肃、吕蒙、陆逊四人死因，发言人2仅概括为东吴内斗严重，双方表述详略不一但无实质冲突。
+# 待探讨问题与后续
+- **未确认**：红楼梦后四十回是否为高鹗所续、其结局是否符合曹雪芹原意，发言人2提出疑问，发言人4解释官方说法是未违背作者原意，但未达成定论。
+- **未定论**：红楼梦人物结局的解读，如探春、史湘云的结局、最后谁与贾宝玉在一起，发言人4指出均为猜测，无明确说法。
+- **未确认**：红楼梦的版本解读，发言人2提到有反清复明说法，称林黛玉代表明朝、薛宝钗代表清朝，发言人4提到秦可卿被解读为前朝公主，均属猜测性解读，未获证实。
+- **待核实**：曹雪芹小道的位置，发言人3称在北京植物园北苑所旁边村子附近，发言人4称植物园内有其故居，具体位置未核实。</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6453/3016</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="13.5" customHeight="1" s="9">
       <c r="A51" s="6" t="inlineStr">
@@ -15240,6 +16944,56 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论围绕三国赤壁之战、合肥之战、火烧连营等战役的军事影响与人物评价展开，由发言人1、发言人2、发言人3共3人参与。讨论由发言人1承接此前《红楼梦》《三国》《水浒》《西游记》《金瓶梅》的系列话题，延伸至三国故事线的兵法和战法角度。议题范围包括：赤壁之战的影响、合肥之战与孙权北伐、火烧连营与陆逊、孙权与刘备等人物评价、关羽张飞等武将能力、曹操五子良将、诸葛亮北伐街亭失守的假设。讨论以分享观点为主，未形成统一结论，整体倾向认为赤壁之战和合肥之战均因双方水陆战能力差异导致僵持，孙权作战能力较弱。关键锚点包括公元215年合肥之战、张辽率800死士大破孙权十万大军、火烧连营七百里。讨论按议题逐块推进，由发言人1主导讲述史实，发言人2、发言人3穿插补充和质疑，整体呈漫谈发散状态。
+# 发言要点
+## 赤壁之战与合肥之战
+- **发言人1**：赤壁之战曹操败因在于军队以虎豹骑为主、擅长陆战，刚收服荆州没有像样水军，不像江东以水军为主，长江过不去；吴军擅长水战但上岸无法与曹军骑兵对抗，双方僵持。
+- **发言人1**：东吴北伐必须过合肥——从建业（今南京）过长江到江北，经小河到巢湖上岸，打下合肥才能靠近淮河继续北进；孙权一生多次攻合肥未果。
+- **发言人1**：公元215年合肥之战，曹军主力在攻汉中，合肥仅张辽、李典、乐进三将镇守且三人矛盾深；张辽率800死士骑马冲锋，孙权大败，留下「张八百大破孙十万」的段子。
+- **发言人1**：合肥之战中孙权在城外扎营准备攻城，张辽率800死士突袭，吴军未反应过来；张辽部通过被俘吴军辨认出孙权（骑术好、射箭准、上身长下身短、留小胡子），后悔差点抓住他。
+- **发言人1**：张辽威震合肥，城内小孩闻其名不敢啼哭；后人吐槽孙权「正面打敌人打不过，偷盟友的家专业」，称「合肥战神孙十万」。
+- **发言人1**：今南京紫金山孙权墓确切位置已找不着，只立碑写「此地可能就是孙权墓的大概位置」，碑前堆满张辽的影视海报和游戏卡片。
+- **发言人2**：小时候看「生子当如孙仲谋」觉得孙权厉害，长大后观感反转，认为他不只是「孙十万」的问题。
+- **发言人3**：孙权在孙十万之前也打过败仗——孙策刚死时，好几万人打人家，被几千人追着打；具体对手名字记不清（非刘表、非张辽，在赤壁之战前）。
+- **发言人1**：追问发言人3所述败仗时期（孙坚时期、周瑜打曹仁时期还是刘琦时期），发言人3未能确认具体对手和战役。
+## 火烧连营与陆逊
+- **发言人1**：刘备因体恤下属，不忍士兵遭酷暑折磨，让军队在密林扎营；陆逊趁秋季干燥、树叶飘落时放火，连营七百里被烧毁，刘备只身逃回白帝城。
+- **发言人2**：质疑陆逊与孙家有仇（「陆家和孙家没听过」）。
+- **发言人1**：陆逊是江东四杰之一；孙策因「小霸王」冒失被刺杀，曹操说「生子当如孙仲谋」是因为孙权虽开疆拓土能力不行，但能守住家业，比曹操几个儿子争气。
+## 三国人物评价
+- **发言人3**：从南往北打（北伐）除朱元璋外不太好找，能守住首都就不错了。
+- **发言人3**：孙权打仗打得不好，刘备至少汉中之战打得挺好。
+- **发言人1**：刘备夷陵之战被仇恨冲昏头脑、冒进失败；汉中之战有法正和黄权辅佐，靠地势把曹操耗出汉中。
+- **发言人1**：关羽个人战力强，阵中斩将是历史第一人做到——直接斩杀对方主将改变战场局势；水淹七军之外还有斩颜良、诛文丑。
+- **发言人3**：关羽「阵中斩将」与黄忠定军山斩夏侯渊不同——关羽是双方摆好阵后斩将，黄忠可能是从山上冲下来。
+- **发言人3**：张飞没有经典战役记录，只知道长坂坡。
+- **发言人1**：张飞在演义里与马超在成都城下大战五百回合。
+- **发言人1**：曹操手下五子良将包括张辽（从吕布降来）、曹仁、夏侯渊、张郃、徐晃、于禁；于禁后来被关羽生擒，曹操「血厚人多」耗得起。
+- **发言人1**：诸葛亮第一次北伐若用魏延守街亭，大概率能把张郃反杀回去，不会像马谡那样轻易丢掉街亭，北伐可能成功；魏延想法大胆但不太符合蜀汉实际支撑。
+- **发言人3**：认同蜀汉地盘太小是制约因素。
+# 共识形成
+- **一致意见**：赤壁之战与合肥之战均因双方水陆战能力差异导致僵持——曹操以虎豹骑为主、擅长陆战，因缺乏水军败于赤壁；东吴擅长水战，上岸后无法与曹军骑兵抗衡，孙权一生多次攻打合肥未果。此判断由发言人1系统阐述，发言人2、发言人3未提出异议。
+- **倾向性认识**：孙权作战能力较弱。发言人1称孙权「开疆拓土能力不行，但能守住家业」，后人称其为「合肥战神孙十万」；发言人2表示「长大以后感觉公平反转得比较厉害」；发言人3补充孙权早期还有败仗，「几万人让人家几千几百人追着打」。
+- **主要分歧点**：对关羽军事能力的评价不一致。发言人1认为关羽「还是很厉害的」，水淹七军、阵中斩将，失败是因「阵营内的队友不争气」；发言人3质疑「他打过啥？我只知道水淹七军」，认为阵中斩将属个人战力而非部队作战。
+- **关键口径**：公元215年合肥之战，张辽率800死士大破孙权十万大军；火烧连营中刘备连营七百里被陆逊一把火烧毁，只身逃回白帝城。
+# 待探讨问题与后续
+- **未确认**：发言人3提到的孙权早期一场败仗的具体对手与战役名称未确认——发言人3称孙权在孙策刚死时期曾以数万人被对方几千人追击，但未能说出对手姓名，发言人与发言人3先后猜测刘表、张辽、曹仁、刘琦等均被否定，最终未定论。
+- **未定论**：关羽阵中斩将是否为历史第一人——发言人3提出关羽「阵中斩将」是历史第一个做到的人，发言人1以黄忠定军山阵斩夏侯渊作对比，发言人3认为两者情况不同（黄忠可能从山上冲下，关羽是摆好阵后斩将），但未形成一致结论。
+- **未定论**：张飞是否有经典战役——发言人3表示只知长坂坡，发言人1补充演义中张飞与马超大战五百回合（成都城下决战），未进一步展开。
+- **未确认**：发言人3提到的孙权早期败仗对手，发言人1曾提出「刘琦时期」的猜测，发言人3未明确确认，话题随即被发言人1以「谢谢」结束并转向下一议题。</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4899/2556</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="13.5" customHeight="1" s="9">
       <c r="A52" s="6" t="inlineStr">
@@ -15295,6 +17049,63 @@
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次专项讨论会由主讲人讲解1979年至1989年的苏阿战争，围绕战争背景与经过、阿富汗战略地位与“帝国坟场”成因、各方援助及苏联撤军原因三个板块展开，并回答听众提问。阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带；其国土90%为高原山地，易守难攻，历史上多次被称为“帝国坟场”。20世纪50年代，阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，国内精英阶层奉行亲英与亲苏并行的政策。1979年12月24日平安夜，苏联以阿富汗请求救援为借口，以兵变政变形式派兵突入阿富汗，一夜控制喀布尔，处决阿明一家，扶植卡尔迈勒上台，将阿富汗纳入苏联阵营。此举招致阿拉伯国家、中国及西方盟国不满，各方合力援助阿富汗抵抗组织。阿富汗抵抗组织与苏联进行长达十年的游击战争，中国援助了五六式冲锋枪和五六式半自动步枪，并派专家教授兵法、地道战、地雷战等战法，但未派兵；美国援助了毒刺导弹等单兵武器，有效压制苏联武装直升机。苏联基层官兵普遍厌战，士气低落，最终于1989年从阿富汗撤军。讨论中，发言人3认为苏联出兵阿富汗是勃列日涅夫逻辑下不允许成员外出的体现，类似出兵捷克，属战略性失误；发言人1补充冷战时期苏攻美守的背景。关于阿富汗难打的原因，发言人1解释其90%地区为高原山地，乡村由部落长老控制，政府控制力弱，天然适合游击战。
+# 核心观点与论证
+## 阿富汗地处亚洲咽喉，为兵家必争之地
+- **地理位置**：阿富汗东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为“亚洲的中间走廊地带”，谁控制了阿富汗谁就控制住亚洲的咽喉。
+- **地形特征**：国土纵深90%为高原山地地带，易守难攻，是天然游击战地区，历史上多次获得“帝国坟场”称号。
+- **资源状况**：阿富汗本身是贫油国，但周边国家如西边伊朗、北边土库曼斯坦和塔吉克斯坦都是富油国。
+## 苏联出兵阿富汗的决策背景
+- **战前态势**：20世纪50年代阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，国内精英阶层奉行亲英与亲苏并行政策，文化上师从英国议会制度与大学现代科学，国家建设和工业方面向苏联看齐。
+- **阿明政权**：基辛格评价阿明“用苏联的火柴点美国的香烟”，两边要好处；后阿明对苏联干涉内政不满并过度导向美国，苏联担心阿富汗脱离掌控会使中亚地区陷入被动。
+- **冷战逻辑**：发言人3指出，按勃列日涅夫逻辑不允许苏联阵营任何成员外出，类似此前出兵捷克，阿富汗是特殊战略要地，苏联必须下场，属**战略性失误**；发言人1补充同期为苏攻美守时期，苏联正进行意识形态扩张与军事霸权恐吓。
+## 苏联入侵经过与各方反应
+- **入侵过程**：1979年12月24日平安夜，苏联趁阿富汗高层与军队被清散信号麻痹，以“阿富汗请求苏联救援”为借口，以兵变政变形式从东部、中部及西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台。
+- **国际反应**：阿拉伯国家、中国及西方盟国共同不满与抵触，合力援助阿富汗；阿富汗伊斯兰狂热圣战者不甘领土被占，各方达成默契——阿富汗和穆斯林国家出兵源，中国和西方盟国出武器与情报资源。
+## 阿富汗抵抗战争与苏联撤军
+- **游击战条件**：除喀布尔、坎大哈等主要城市外，90%地区为乡村部落长老制，政府无控制力，各村落部落各自为政，任何列强及城市政府无法有效控制广大高原山地。
+- **中国援助**：援助五六式冲锋枪和五六式半自动步枪（与AK47同型号），派专家教授地道战、地雷战等抗战战法，未派兵；同时稀释国内饱和军工业，与西方盟国达成秘而不宣的默契。
+- **美国援助**：提供毒刺导弹等先进单兵武器，有效压制苏联最先进的雌鹿武装直升机；坦克和步兵战车在高原山地无法形成有效战斗力，需以步兵加武装直升机作战。
+- **苏联败因**：军事实力看似庞大但武器发挥不了作用，基层官兵普遍厌战、士气一落千丈，最终扛不住阿富汗人民战争的消耗，于1989年撤军。
+# 金句总结
+&gt; “谁控制了阿富汗，谁就控制住了亚洲的咽喉。”
+- 背景：回答听众关于阿富汗为何被多国觊觎的提问，点明其地理位置的关键性。
+&gt; “阿富汗多次获得其帝国坟场的称号。”
+- 背景：讲述阿富汗历史时，概括列强入侵阿富汗屡遭失败的结局。
+&gt; “他是用的苏联的火柴在点的美国的香烟。”
+- 背景：引基辛格对阿富汗国王阿明的评价，形容其同时向苏联与美国两边要好处的墙头草姿态。
+&gt; “阿富汗是一个名副其实的兵家必争之地。”
+- 背景：介绍阿富汗地处亚洲中部、连接多国的地理位置时所作判断。
+&gt; “任何一个列强以及阿富汗的城市政府对于广大的阿富汗高原山地地区无法形成一个有力的控制。”
+- 背景：解释阿富汗难打的原因，指出其90%国土为高原山地、乡村由部落长老各自为政。
+# Q&amp;A 环节
+**听众**：阿富汗到底有啥好呀？为啥都想打它？
+**主讲人**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+**听众**：是不是阿富汗有石油啊？
+**主讲人**：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
+**听众**：其实这个我感觉得用当时的冷战思维来看，因为阿富汗当时被苏联化为苏联势力中的一员。根据勃列日涅夫的逻辑，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，加上苏联这个错判，导致苏联大大的战略性失误。
+**主讲人**：对的，同时期冷战状态也是苏攻美守时期，苏联咄咄逼人地进行意识形态扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
+**听众**：之前看阿富汗那边把部队叫什么圣战者，这个是什么意思？
+**主讲人**：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民那样不顾一切、抱着同归于尽的思想进行圣战。
+**听众**：这次苏阿战争之前，已经有三次英阿战争，阿富汗被称为帝国坟场，能不能简单说一下为什么这个位置这么难打？虽然它的国土面积没有那么大，经济实力又没有那么好。
+**主讲人**：因为这个国家百分之九十都是高原山地地带，是天然的游击战地区。除了喀布尔和坎大哈那几个主要城市以外，剩下大部分百分之九十的地区都是乡村部落长老制，政府没有任何控制力，由部落长老控制，各个村落与部落各自为政，导致任何列强以及阿富汗城市政府都无法对广大高原山地形成有力控制。当时咱们国家也帮助阿富汗圣战抵抗者，教他们抗战时期用的地道战、地雷战等战法，和苏联持续进行游击战争；美国同时期援助了比较先进的单兵武器，比如毒刺防空导弹，可以有效压制苏联当时最先进的雌鹿武装直升机。坦克和步兵战车在阿富汗无法形成有效战斗力，因为这些装备主要用于平原地带，高原山地还是要以步兵加武装直升机才能形成有效战斗力。苏联军事实力看似庞大，但武器发挥不了作用，基层官兵普遍厌战，士气一落千丈，最终1989年扛不住压力撤军。
+**听众**：咱们男生基本都说完了，都说过一遍了。
+**主讲人**：也是给了一些枪炮，比如咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，通过援助形式把咱们国家已经饱和的军工业产业稀释掉，同时也是为了抵抗苏联霸权主义和西方盟国达成秘而不宣的默契。
+**听众**：只提供军火，但是没有派人。
+**主讲人**：专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3129/3150</t>
         </is>
       </c>
     </row>
@@ -15484,6 +17295,66 @@
           <t>小组讨论</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论为多人漫谈式闲聊，共4位发言人（发言人1、2、3、4），从东野圭吾《白夜行》的悬疑叙事与阴暗结局切入，结合《菊与刀》分析日本文学中的民族性格，随后围绕各国文学特点与底层描写展开比较，议题范围涵盖日本、法国、英国、俄国、美国文学特点，中国底层文学与电影（如《平凡的世界》、台湾电影《假如我是真的》），以及《西游记》狮驼岭章节的黑暗寓意及其对佛教的批判。讨论以分享观点为主，未形成统一结论，整体按议题逐块推进，由发言人2多次引导话题转向，从日本文学延伸至各国文学比较，再转入中国底层文学与《西游记》的黑暗描写，发言较为发散。
+# 发言要点
+## 日本文学《白夜行》
+- **发言人1**：《白夜行》是悬疑小说，叙事手法新颖，上来都是隐藏线索，一直猜不到真相，每个人都有嫌疑，但结局非常阴暗。
+- **发言人2**：美国作家本尼迪克特《菊与刀》生动描绘日本人性格特点，《白夜行》中也能体现，符合日本形象。
+## 各国文学特点比较
+- **发言人2**：法国文学有浪漫的理想主义精神和奉献，在《悲惨世界》中体现生动；雨果作品值得一读。
+- **发言人4**：法国文学描绘底层民众较多，英国小说多是贵族生活。
+- **发言人1**：法国有抗争精神，因为法国确实革命了很多次；英国想维持贵族秩序。
+- **发言人2**：比较法国与俄国哪个描绘底层民众更生动。
+- **发言人4**：俄国文学戏剧性更明显、更曲折。
+- **发言人2**：个人喜欢契诃夫，如《变色龙》《装在套子里的人》《凡卡》；苏联时期喜欢格罗斯曼《命运与生活》，他是红军战地记者，写红军后期进入欧洲后看似不公的问题，从平民视角看苏联红军基层真实形象。
+- **发言人2**：《古拉格群岛》真正批判人性黑暗面，最早出版版本是法语版，俄语版要等苏联解体后才发行。
+- **发言人1**：苏联作者虽多但看得少，高尔基因正面宣传看得较多。
+- **发言人1**：英国讲底层的也很多，如《圣诞欢歌》《雾都孤儿》，写贵族与穷人之间的鸿沟，穷人把希望寄托在宗教或虚无的东西上。
+- **发言人2**：英国土地承载不了人口膨胀，以英国、爱尔兰为主移民北美新大陆。
+- **发言人2**：美国文学历史短，叙事风格不同于欧洲，更多表现现代社会，与欧洲理想主义精神图腾差别较大。
+- **发言人1**：美国历史太短，美洲大陆没发生欧亚大陆那么多悲惨事件，相对幸福；提到《了不起的盖茨比》。
+- **发言人2**：北美大平原农业资源广阔，美国永远不缺粮食；欧亚大陆的瘟疫、大饥荒在美国从未发生过，美国人无法真正理解饥荒为何物。
+- **发言人2**：俄国文豪如列夫·托尔斯泰是前线俄军，把百姓疾苦与贵族奢华对比讽刺；因沙俄新闻管制严厉，以小说方式发表，俄国文学对人性丑恶的揭露与批判更为讽刺。
+- **发言人1**：初中高中时读中英对照英语读物，光看汉语部分就觉得名著很有意思。
+## 中国底层文学与电影
+- **发言人1**：国内写底层的作品其实挺深刻，如《平凡的世界》，但很多因政策原因不让看，以前根据底层小说改编的电影也不让看。
+- **发言人2**：台湾电影《假如我是真的》改编自俄国果戈里《钦差大臣》，结合文革知青上山下乡真实事件，上世纪七十年代末八十年代初拍摄。
+- **发言人2**：当时台湾与大陆搞舆论宣传战、意识形态攻略，台湾把大陆上山下乡、文革时期的不公通过电影批判出来。
+- **发言人2**：日本人能打垮国民党军队，是因为日本人给灾民发放粮食，国民党对灾区视而不见，导致日本人占领河南省大部地区。
+- **发言人1**：有人为换取粮食给日本人送情报，这是人性，没办法。
+- **发言人2**：高尔基《海燕》是老百姓被压迫久了之后的呐喊和奋起反抗，体现尤为明显。
+## 《西游记》狮驼岭章节
+- **发言人2**：《西游记》以小说形式揭露佛教世界的虚伪，狮驼岭章节尤为突出——佛门三大圣兽青狮、白象、大鹏偷离佛门到下界作妖，把城池所有人全部吃掉，扶植小妖成为国家公民。
+- **发言人2**：原著描写孙悟空路过时尸骸遍地、不战而弃；人皮当毯、骷髅头骨当装饰物和器具，此地距灵山仅500公里左右，却发生如此人伦惨剧，与佛门普度众生、众生平等大相径庭。
+- **发言人2**：吴承恩在古代就预测并批判揭露佛教被上层王公大臣用来迷惑底层民众、进行高压奴役统治，而非真正众生平等；并联系旧西藏状况，称共产党解放西藏避免了悲剧延续，这是汉传佛教与藏传佛教的根本区别。
+- **发言人4**：问狮驼岭是不是没拍到电视剧。
+- **发言人2**：有拍，但没把那些惨烈细节讲得那么生动。
+- **发言人1**：电视剧只拍几个妖精被孙悟空全干掉，没讲那么生动。
+- **发言人1**：《黑神话悟空》没有设计狮驼岭那一章，估计不太好设计，太血腥、不好过审，且意义深刻，剧情既要委婉又要深刻很难。
+- **发言人2**：狮驼岭章节中如果不是佛祖出手，孙悟空终究要被大鹏精打败；大鹏精是《西游记》全剧中唯一能遛猴子的反派角色。
+# 共识形成
+- **一致意见**：与会者普遍认同《白夜行》叙事手法新颖、结局阴暗，符合日本文学特点；法国文学体现抗争精神与浪漫理想主义（如《悲惨世界》），英国文学多写贵族生活、底层描写较少，俄国文学对底层民众的描写更生动且戏剧性明显，美国文学历史短、多表现现代社会，与欧洲理想主义不同。
+- **倾向性认识**：发言人2认为《西游记》狮驼岭章节揭露佛教虚伪，吴承恩借此批判佛教被上层王公大臣用来迷惑、奴役底层民众，并联系旧西藏状况；发言人1、发言人4未提出反对，仅就电视剧未生动呈现原著细节、游戏《黑神话悟空》未设计该章节（因过于血腥且意义深刻）进行补充。
+- **主要分歧点**：发言人1认为国内底层文学（如《平凡的世界》）写得深刻但因政策原因受限；发言人2未直接回应，转而举例台湾电影《假如我是真的》改编自俄国《钦差大臣》并结合文革知青上山下乡真实事件，属当时两岸舆论宣传战的一部分，双方未就国内底层文学受限程度达成一致。
+# 待探讨问题与后续
+- **未确认**：发言人2提到《古拉格群岛》最早出版版本为法语版、俄语版在苏联解体后才发行，此说法未获其他成员回应或核实。
+- **未确认**：发言人2称《假如我是真的》改编自俄国小说《钦差大臣》并结合文革知青上山下乡真实事件，发言人3询问剧情后发言人2未完整展开，仅说明涉及知青上山下乡时期真实体现。
+- **未定论**：发言人1提出国内底层文学（如《平凡的世界》）因政策原因受限、相关电影也不让看，此观点未获其他成员明确认同或反驳，讨论随即转向其他话题。
+- **未确认**：发言人2称《西游记》狮驼岭章节中孙悟空不战而弃、若非佛祖出手将被大鹏精打败，并称大鹏精是全书唯一能遛猴子的反派角色，此判断未获其他成员回应。
+- **未定论**：发言人2将狮驼岭描写与旧西藏状况、汉传佛教与藏传佛教本质差异相联系，发言人1仅回应「确实挺吓人」，未就此观点展开讨论或达成一致。</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5886/2910</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="13.5" customHeight="1" s="9">
       <c r="A54" s="7" t="inlineStr">
@@ -15549,6 +17420,96 @@
       <c r="B54" s="7" t="inlineStr">
         <is>
           <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议为手机图库项目团队例会，由产品经理（发言人1）主持，产品（发言人2）、开发1（发言人3）、开发2（发言人4）参与，围绕项目整体进展、排期与风险对齐展开。会议覆盖智能分类与相册推荐改版、AI智能标签接口性能、同步模块与内存管理、缩略图渲染优化、时间轴加载优化、AI修图功能预留及项目里程碑等议题。关键结论包括：隐私相册入口提升至首部顶部二级菜单；AI标签采用本地缓存策略并叠加端侧预过滤方案；同步模块采用分片加载方案；时间轴采用本地索引预加载；AI修图本次不实现但预留插件化架构；里程碑按原定计划月底封版，内测包暂定下周三发布。关键数字锚点：AI识别模型准确率提升约88%、单次请求耗时从800毫秒涨至约1.5秒、内存占用降约30%、主流机型帧率稳定60帧。
+# 分段速览
+## 00:00:00-00:01:23 开场与产品侧交互迭代同步
+会议开场，产品经理说明会议目的为同步手机图库项目进展、对齐排期与风险。产品侧汇报近两周推进智能分类和相册推荐改版，高保真原型已出V1.5版，调整了网格视图交互逻辑与长按微动效；测试反馈低端机上滑列表偶发掉帧，已与开发2沟通通过降低预览图缩放级别换帧。用户调研收到隐私相册入口太深的吐槽，建议下一版将入口提升至首部顶部二级菜单，产品经理确认该改动不算大，要求出交互方案评审，并强调掉帧问题需抓紧，因下周将进入性能压测。
+## 00:01:51-00:03:19 AI智能标签接口与同步模块问题
+开发1汇报AI智能标签V2识别模型已跑通，准确率较上一代提升约88%，但增加视频帧提取功能后单次请求耗时从800毫秒涨至约1.5秒。产品反对异步推送方案，提出本地缓存策略，开发1确认可行并预计三天联调完，但提示缓存命中率低时需回溯。开发1同时反馈云同步断点续传在弱网环境下出现状态机紊乱；开发2补充同步队列积压超1000张时部分机型出现OOM崩溃，已加分片加载机制每次拉50张，但拖慢同步进度，提出申请后台静默同步权限或允许手动设置同步频率。
+## 00:03:57-00:05:03 同步方案定调与缩略图渲染优化
+产品经理判断后台同步权限审核严、大概率下不了，决定先按分片加载方案走但进度不能拖。开发2汇报缩略图渲染优化进展：采用新图片解码库将JPEG硬解换软解，内存占用降约30%但CPU占用上升，主流三款机型灰度帧率稳定60帧、低端机约50帧，周四性能报告今晚出初稿。另发现批量删除照片同时触发回收站重建索引时数据库偶发锁死，已用消息队列排队处理临时规避，正式修复排进V1.2迭代。
+## 00:05:03-00:07:01 端侧预过滤与按需加载方案
+产品经理提出端侧预过滤思路：先用轻量级模型过滤gif或截图，再走全量云端识别，可平均压耗时一半。开发1认可该思路，提出端侧推理需再申请200兆本地缓存空间，产品评估安装包体积影响后认为问题不大，建议做成按需加载——用户首次进入智能标签时才触发下载。开发1确认用现有资源下发模块可实现，约两天搞定，将拉上开发2配合端侧推理联调。开发1另反馈时间轴视图滑动到二十年前老照片时页面卡死三秒以上，原因是EXIF解析耗时与磁盘IO瓶颈，计划加本地索引预加载。
+## 00:07:01-00:09:15 时间轴预加载与AI修图预留
+产品经理同意时间轴预加载方案，提醒注意别与云同步模块抢资源。开发2确认预加载放主线程IO池、同步放子线程后台服务，互不影响，但预加载需用户授权媒体和存储权限，若拒绝需引导弹窗，产品明天出稿走柔和提示路线。产品同步运营希望下版本加AI修图快捷入口（一键去背景、智能调色等），产品经理判断本次主线是性能和分类、硬塞风险大，决定在PRD中预留接口和UI占位，开发侧做成插件化架构。开发2提出趁此重构图片处理管线，用GLSL写统一接口，工作量多一周。
+## 00:09:42-00:12:18 优先级调整与里程碑确认
+产品经理调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化，要求开发2今天下班前评估精确工作量、开发1排联调时间赶在周五前跑通主干流程，周四性能压测需拿达标数据。里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块。开发1今晚搭好接口联调环境并拉群与DBA对齐索引策略，开发2今晚继续跑压测数据、明天同步，并确认性能报告将iOS和安卓对比数据分开列、由测试组合并成一份总览。
+# 要点梳理
+## 智能分类与相册推荐改版
+- **高保真原型**：已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈。
+- **掉帧问题**：低端机上滑列表偶尔掉帧，已与开发2沟通，拟通过降低预览图缩放级别换帧。
+- **隐私相册入口**：用户调研反馈入口太深，产品经理确认提升至首部顶部二级菜单，不算大改动，需出交互方案评审。
+## AI智能标签接口与性能优化
+- **识别模型**：V2版已跑通，准确率较上一代提升约88%。
+- **请求耗时**：因增加视频帧提取功能，单次请求耗时从800毫秒涨至约1.5秒。
+- **本地缓存策略**：产品反对异步推送，确定先做本地缓存，首次识别慢、之后本地读库秒出；开发1下午拉分支改逻辑，预计三天联调完；缓存命中率低时需回溯。
+- **端侧预过滤**：先用轻量级模型过滤gif或截图，再走全量云端识别，可平均压耗时一半；开发1评估模型体积和端侧推理开销，需申请200兆本地缓存空间，产品评估安装包体积影响。
+- **按需加载**：用户第一次进图库智能标签时才触发下载，平时不占空间；开发1用现有资源下发模块实现，预计两天搞定。
+## 同步模块与内存管理
+- **断点续传**：云同步模块在弱网环境下出现状态机紊乱。
+- **OOM崩溃**：同步队列积压超1000张时部分机型崩溃，iOS内存回收机制较激进。
+- **分片加载**：开发2已加机制，每次只拉50张，处理完再拉下一批；会拖慢同步进度。
+- **后台同步权限**：审核较严，大概率下不了，决定先按分片加载方案走。
+## 缩略图渲染与性能评审
+- **解码库优化**：JPEG硬解换软解，内存占用降约30%，CPU占用上升。
+- **灰度数据**：主流三款机型帧率稳定60帧，低端机约50帧；周四过性能评审，性能报告今晚出初稿。
+- **数据库锁死Bug**：批量删除照片同时触发回收站重建索引时偶发，已用消息队列排队临时规避，正式修复排进V1.2迭代。
+## 时间轴视图加载优化
+- **卡死问题**：滑动到二十年前老照片时页面卡死三秒以上，测试提了三个高优Bug。
+- **根因**：历史图片EXIF解析耗时太长，加上磁盘IO瓶颈。
+- **预加载方案**：最近三个月照片建树状结构，滑到底部动态加载旧数据；预加载放主线程IO池，同步放子线程后台服务，互不冲突。
+- **权限引导**：预加载需用户授权媒体和存储权限，若拒绝需引导弹窗；产品明天出稿，走柔和提示路线，不用强制遮罩。
+## AI修图功能预留
+- **需求来源**：运营反馈希望下版本加AI修图快捷入口（一键去背景、智能调色等）。
+- **本次范围**：主线是性能和分类，硬塞风险大；在PRD中预留接口逻辑和UI占位，开发侧做成插件化架构，后端按标准RESTful加Swagger文档。
+- **管线重构**：开发2建议趁重构把渲染层抽成插件化，用GLSL写统一接口，工作量多一周；产品经理调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化。
+## 项目里程碑与内测计划
+- **封版时间**：里程碑按原定计划，月底封版。
+- **内测安排**：内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块；产品做好反馈收集表，开发准备好日志抓取工作。
+## 结论与决定
+- 隐私相册入口提升至首部顶部二级菜单，产品经理评审交互方案。
+- AI标签采用本地缓存策略，开发1下午拉分支改逻辑，预计三天联调完。
+- 端侧预过滤方案通过，开发1评估模型体积和端侧推理开销，产品评估安装包体积影响。
+- 按需加载方案通过，开发1用现有资源下发模块实现，预计两天搞定。
+- 同步模块采用分片加载方案，不申请后台同步权限。
+- 缩略图渲染优化采用新解码库，临时规避方案先稳住，正式修复排进V1.2迭代。
+- 时间轴加载采用本地索引预加载方案，开发2负责实现，注意与云同步资源隔离。
+- AI修图本次不实现，在PRD中预留接口和UI占位，开发侧做成插件化架构。
+- 图片处理管线重构为插件化，用GLSL统一接口，开发2评估工作量今天下班前发产品经理。
+- 非核心UI微调往后排，资源给到管线重构和AI标签优化。
+- 里程碑按原定计划月底封版，内测包暂定下周三发。
+## 行动项与分工
+- **产品经理（发言人1）**：评审隐私相册入口交互方案；周四下午两点参加UI走查；要求测试组将iOS和安卓性能报告合并成一份总览；调整优先级，非核心UI微调往后排。
+- **产品（发言人2）**：下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查；制作AI修图占位图；十一点半前将UI走查稿发给产品经理；做好内测反馈收集表。
+- **开发1（发言人3）**：下午拉分支改AI标签本地缓存逻辑，预计三天联调完；评估端侧预过滤模型体积和端侧推理开销；用现有资源下发模块实现按需加载，预计两天搞定；排联调时间赶在周五前跑通主干流程；今晚搭好接口联调环境，明天与测试过一遍；拉群与DBA对齐索引策略。
+- **开发2（发言人4）**：实现时间轴本地索引预加载，注意与云同步资源隔离；评估图片处理管线重构工作量，今天下班前发产品经理；今晚继续跑分片加载和渲染优化压测数据，明天同步；让测试组将iOS和安卓性能报告合并成一份总览。
+## 待确认与风险
+- 端侧预过滤的模型体积和端侧推理开销待评估。
+- 本地缓存命中率低时的回溯方案待确认。
+- AI修图功能的接口逻辑和UI占位需在PRD中明确。
+- 图片处理管线重构的具体工作量待开发2评估。
+- 低端机上滑列表掉帧，影响用户体验。
+- AI标签单次请求耗时从800ms涨到1.5s，可能影响用户等待体验。
+- 云同步断点续传在弱网下状态机紊乱。
+- 同步队列积压超1000张时部分机型OOM崩溃。
+- 批量删除时数据库锁死，临时规避但正式修复排到下下版本。
+- 时间轴滑动到老照片时卡死三秒以上，影响核心功能体验。
+- 预加载需用户授权媒体和存储权限，若拒绝可能影响功能。
+- 后台同步权限审核严，可能无法实现后台静默同步。
+- 管线重构工作量增加，可能影响其他任务进度。</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3605/4386</t>
         </is>
       </c>
     </row>
@@ -15632,6 +17593,81 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次月度研讨会由总监主持，组长、销冠、销售A、销售B参加，围绕上月销售数据复盘与下月去化目标展开。上月案场总到访320组，环比增15%；成交76套，转化率23%，较上月降4个百分点；渠道带看占比65%，自然来访35%；蓄客量约3200组，认购到成交流失率约18%。总监指出量够但转化不足，客户流失主因价格预期与交付信心。会议确定多项动作：工地开放日定于每周三固定开放并提前推送；逼定权益可视化并更新物料；渠道带看实名登记；下月总去化目标120套，其中销冠28套、三人组50套、机动12套；周末办业主答谢会联动去化；安排两次专项培训；销控实时同步并问责；财务法务周末值班；邀约话术统一为“老业主专属品鉴宴”。总监强调跟进提速、客户不过夜，安排回访未成交300多组客户，渠道部由总监亲自沟通。
+# 分段速览
+## 00:00:00-00:01:17 开场与上月数据复盘
+总监开场说明会议定于下午两点至两点四十，共四十分钟，指出上月市场波动大、项目整体去化尚可但部分数据不理想。组长汇报后台完整数据：上月案场总到访三百二十组，环比增加百分之十五，达标；成交七十六套，转化率百分之二十三，较上月百分之二十七下降；渠道带看占比百分之六十五，自然来访百分之三十五；蓄客量约三千二百组，认购到成交流失率约百分之十八。总监总结为量够但卡在逼定和转化环节，并指出渠道带看比例偏高意味着自主拓客和案场拦截能力在退化。
+## 00:01:53-00:03:36 客户流失抗性分析与工地开放日提议
+销冠复盘上月流失客户，集中在两个抗性：价格预期方面竞品推特价房、首付分期或送物业费，客户有落差；交付信心方面客户关注园林选材、地下车库层高、外墙保温层等细节，需将工地实时进展和材料样板直接呈现。销售A补充称带改善型客户看房时请施工经理和工人直接答疑，客户认可工程透明才成交，但工地开放日频率不够、陪看占时间。组长反馈开放日流程繁琐、报备审批需半天，建议设固定节点每周三下午开放，提前在客户群和朋友圈预告。总监认可并要求组长出方案，定于每周三、提前两天在CRM系统推送意向客户。
+## 00:04:22-00:06:12 价格抗性逼定策略与物料更新
+总监提出下月政策调整，特价房名额有限，可在装修包和车位上做文章，并询问销冠送三年物业费的逼定手法。销冠说明采用算总账方式：不直接降价，而是将物业费、车位管理费、装修损耗拉表对比竞品，说明单价虽高两千但十年省下物业和品质维修费，再递上"限时权益"逼定函，承诺本周定可申请多送三年物业费。销售B提出客户对"限时权益"不买账，需将权益具象化，如打印三年缴费明细放在合同旁，并反映案场物料更新慢、逼定函常为上月版本。组长记录物料问题，联系设计本周出新版，并计划下月制作"权益可视化"台卡放洽谈区。
+## 00:06:12-00:09:10 跟进节奏提速与渠道实名制
+总监强调客户不过夜，安排组长带销售A和销售B回访上周未成交的三百多组客户，重点盯"再考虑考虑"的；销冠梳理手头二十几个高意向客户，看能否周末逼定。针对渠道无效带看多，总监决定下月起带看必须实名登记并有明确需求标签，否则扣减渠道积分。销售A反映中介可能抵触，总监表示渠道部由自己沟通，质量大于数量底线不能破。销售B汇报老带新政策已下来，成功一套奖励两万现金或等值车位券，本月推四组、两组在谈，老业主需话术和礼品支持。组长准备定制伴手礼（高端茶叶礼盒、保温杯），销冠建议搞"业主推荐官"活动，成功推荐可升级物业服务等级、优先预约维修、免费家政清洗一次。
+## 00:09:46-00:11:20 下月目标分解与周末答谢会
+总监传达集团下月总去化一百二十套指标，比上月多百分之五十。组长按人员配置和上月产出权重拆分：销冠目标二十八套，组长、销售A、销售B三人一组共五十套，剩余十二套作为机动和渠道攻坚储备。销售A表态手头有十五个准客户等认筹通知，配合组长资源倾斜可扛住，希望渠道带看质量再筛一筛；销售B计划周末办小型业主答谢会，邀请成交业主分享并推老带新政策。销冠表示可协助盯两桌，其改善型客户与答谢会客群重合度高，可做联动集中去化。总监明确分工：销冠带人协助、销售B主抓流程、销售A负责客户邀约和逼定记录。
+## 00:11:20-00:15:07 培训安排、销控纪律与收尾补充
+总监安排本周两次专项演练，分别为"竞品对比与抗性化解"和"逼定时机与谈判心理学"，每人必须参加、课后现场抽考、不过加练，组长盯进度并安排签到考核表挂钩下周绩效系数。组长提出销控表更新延迟易引起客诉，总监要求销控实时同步、CRM系统锁房，再出现丢单或客诉直接问责，组长设专人每小时刷新销控大屏。组长总结五项核心议题：工地开放日周三固定开放、逼定权益可视化、渠道带看实名制、周末答谢会联动、专项培训与销控纪律。销售A建议邀约话术统一为"老业主专属品鉴宴"避开"促销"字眼，销售B随即修改短信和电话模板；销冠建议财务和法务在洽谈区待命，现场签单出收据可提升成交率至少两成，总监协调财务法务周六日轮流值班。总监要求组长散会后半小时内发会议纪要和任务分解表，销冠下周晨会分享逼定案例。
+# 要点梳理
+## 上月销售数据复盘
+- **整体数据**：上月案场总到访320组，环比增加15%；成交76套，转化率23%，较上月27%下降4个百分点。
+- **来访结构**：渠道带看占比65%，自然来访仅35%；蓄客量约3200组，认购到成交流失率约18%。
+- **流失原因**：主要集中在价格预期（竞品推特价房、首付分期、送物业费等）和交付信心（客户细问园林选材、地下车库层高、外墙保温层）两个抗性。
+- **总监判断**：量够但转化不够，渠道带看比例高意味着自主拓客能力和案场拦截能力在退化，卡点在逼定和转化环节。
+## 工地开放日标准化
+- **现状问题**：工地开放日频率不够，客户自行看房不便，销售陪看占时间；报备审批流程繁琐需半天。
+- **决定**：工地开放日定于每周三下午固定开放，提前两天在CRM系统推送意向客户，客户直接对接专属顾问，不走复杂流程。
+- **依据**：销售A分享改善型客户案例，带客户三次看工地并直接问工人，客户因工程透明才成交。
+## 价格抗性与逼定策略
+- **算总账法**：销冠不直接降价，而是拉表对比物业费、车位管理费、装修损耗，说明单价虽高2000元但十年省物业和品质维修维护费。
+- **限时权益**：销冠递送“限时权益”逼定函，承诺本周定下来亲自向营销总申请多送三年物业费，过了本周就没有。
+- **权益具象化**：销售B建议把三年缴费明细打印出来放在合同旁，客户更有底；现场物料更新慢，逼定函常是上月版本。
+- **决定**：组长联系设计本周出新版物料，把权益条款写清楚避免歧义；下月做“权益可视化”台卡放洽谈区。
+## 跟进节奏与渠道管理
+- **跟进问题**：客户周末来看，平时销售打电话或整理资料，客户晚上问政策回复慢热度下降。
+- **回访安排**：总监强调“客户不过夜”，组长带销售A和销售B回访上周未成交的300多组客户，重点盯“再考虑考虑”的。
+- **渠道实名制**：下月起带看必须实名登记并有明确需求标签，否则扣减渠道积分；渠道带看量上去了但无效带看太多，中介随便拉人凑数。
+- **渠道沟通**：销售A担心查太严渠道不愿推项目，总监表示渠道部由他亲自沟通，质量大于数量底线不能破，带看质量不行直接换备选。
+## 老带新与业主答谢会
+- **奖励政策**：老带新成功一套奖励两万现金或等值车位券；销售B本月推4组，2组在谈。
+- **伴手礼支持**：组长准备定制高端茶叶礼盒和保温杯，老业主转介绍时直接送。
+- **业主推荐官**：销冠建议每成功推荐一套不仅有钱，还可升级物业服务等级（优先预约维修、免费家政清洗一次），软性权益更易在小区群传播。
+- **周末答谢会**：销售B主抓流程，销售A负责客户邀约和逼定记录，销冠带人协助盯两桌；邀约话术统一为“老业主专属品鉴宴”，避开“促销”字眼。
+## 下月目标与任务分解
+- **总目标**：集团下指标下月总去化120套，比上月多50%。
+- **拆分**：销冠目标28套；组长、销售A、销售B三人一组目标50套；剩余12套作为机动和渠道攻坚储备。
+- **表态**：销售A手头有15个准客户等下周认筹通知，希望渠道带看质量再筛一筛；销售B计划周末业主答谢会推老带新政策。
+## 培训与销控纪律
+- **专项培训**：本周安排两次演练——“竞品对比与抗性化解”“逼定时机与谈判心理学”，每人必须参加，课后现场抽考，过不了加练。
+- **考核挂钩**：组长安排签到和考核表，结果直接挂钩下周绩效系数。
+- **销控问题**：销控表更新延迟，客户定了之后销售还在推同套房子，容易引起客诉。
+- **销控纪律**：销控必须实时同步，谁推哪套在群里喊一声，CRM系统同步锁房；再出现丢单或客诉直接问责，组长设置专人每小时刷新销控大屏。
+## 结论与决定
+- **核心判断**：上月量够但转化不足，卡在逼定和转化环节，需重点提升逼定与转化。
+- **已拍板事项**：工地开放日每周三固定开放；逼定权益可视化并更新物料；渠道带看实名制与质量考核；下月去化目标120套及拆分；周末业主答谢会联动；两次专项培训强制参加；销控实时同步并问责；财务和法务周六日轮流值班在案场外围待命；邀约话术统一为“老业主专属品鉴宴”。
+## 行动项与分工
+- **组长**：出工地开放日标准化方案（每周三、提前两天CRM推送）；带销售A和销售B回访上周未成交300多组客户；准备定制伴手礼；推进“业主推荐官”活动，下周前出详细执行表；安排培训签到考核表；设专人每小时刷新销控大屏；散会后半小时内发会议纪要和任务分解表到工作群。
+- **销冠**：梳理手头二十几个高意向客户，周末一波逼定；协助周末答谢会盯两桌；下周晨会分享逼定案例。
+- **销售A**：梳理客户池（15个准客户）；负责答谢会客户邀约和逼定记录；配合组长回访未成交客户。
+- **销售B**：主抓答谢会流程；修改邀约短信和电话模板为“老业主专属品鉴宴”；准备逼定权益具象化物料。
+- **总监**：协调财务和法务周六日轮流值班；亲自与渠道部沟通实名制事宜；盯渠道和工程对接。
+## 待确认与风险
+- **渠道抵触风险**：渠道方称别的楼盘不查实名制，查太严可能不愿推项目，需总监与渠道部沟通确认。
+- **物料滞后风险**：逼定函等现场物料更新慢，常为上月版本，可能影响逼定效果。
+- **销控客诉风险**：销控不同步可能导致丢单或客诉，已定问责纪律。
+- **答谢会待细化**：业主答谢会的具体流程和物料尚未细化。</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4211/4425</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="13.5" customHeight="1" s="9">
       <c r="A56" s="7" t="inlineStr">
@@ -15703,6 +17739,79 @@
           <t>通用纪要</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次团队例会由组长主持，A与B两位成员参与，围绕ASR模型迭代进度、线上推理延迟及长音频解码卡死问题展开。会议覆盖数据清洗与模型训练、推理延迟优化、长音频卡死修复、监控面板与CI流水线建设、前端采样率升级等议题。关键结论包括：确认流式RNN-T混合架构与2秒切分方案，由A和B分头推进；长序列解码卡死问题由B周四提测热修复版本；前端32k采样率升级由组长拉会推进；监控面板与CI流水线本周内定稿。组长明确稳定性优先、精度次之，下周先出热修复版本上灰度。关键数字锚点：有效语音时长占比提升至94%、WER下降0.8个点、首字延迟目标控制在80ms以内、下周划拨三块A100算力。
+# 分段速览
+## 00:00:00-00:01:21 数据清洗与模型训练进展
+会议开场后，A汇报数据清洗流水线已完成第二轮，有效语音时长占比从89%提升至94%，并重新校对了CTC的blank token分布。B反馈验证集WER下降0.8个点，但低资源语言混合边界场景下切分仍有毛刺，中英文切换时易吞音或重复解码。A确认问题源于CTC对齐阶段对跨语言边界和轻声尾音处理不够平滑。
+## 00:01:21-00:04:35 架构调整与推理延迟优化
+A提出将全纯Transformer架构换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练，并引入MixUp和Cut增强策略。B评估了RNN-T缓存与显存占用风险，A回应计划做INT8量化配合动态缓存释放，压测数据明天下午发群。B提出将动态Batching改为静态分段加流式解码：音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，目标首字延迟控制在80ms以内、吞吐量稳定在120路并发，下周拉线上流量回放做端到端对比。
+## 00:04:35-00:06:43 组长定调与CI流水线
+组长确认方向可行，提出三点要求：流式架构切换不得影响非流式离线批处理、VAD阈值由B做消融实验画曲线找最优解、下周划拨三块A100做增量训练但需与NLP组错峰。A提出用GitLab CI搭建自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码、结果对比，WER未降或RTF超标直接打回，预计三天落地、周四前出V1版本；B配合将压测数据输出为标准JSON格式。
+## 00:06:43-00:08:49 长音频解码卡死问题
+B报告线上出现超长连续带方言口音音频导致解码器loop卡死并触发服务器节点重启，根因是RNN-T的attention权重震荡未收敛。A建议加early stopping机制：连续30步置信度低于0.2时强制截断并返回当前序列，可解决90%以上卡死问题。组长指示稳定性优先、精度次之，下周先出热修复版本上灰度，B负责改解码逻辑、周四提测，A配合长序列数据配比和边界用例验证。
+## 00:08:49-00:11:06 监控面板与前端采样率升级
+B申请接入Prometheus和Grafana监控面板，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标，告警分P0/P1两级，明天下班前发指标定义文档。前端SDK采样率仍为16k而新模型为32k，上采样会引入高频伪影，前端排期推至下月；组长计划拉产品和技术总监优先插队，备选方案为服务端加实时重采样模块，B先出对比文档和插件实测，CPU开销控制在5%以内再提方案。
+## 00:11:06-00:11:57 总结与收尾
+组长总结四项要点：流式RNN-T混合架构和2秒切分方案本周五前出详细设计和压测数据；VAD阈值和长序列解码卡死问题B周四出消融报告和热修复方案；前端32k采样率升级由B出对比文档和重采样插件实测；监控面板和CI流水线本周内定稿并开始对接运维和测试环境。A确认周三前发CI脚本和测试用例评审，B确认盯推理优化、VAD消融、热修复和监控文档，会议结束。
+# 要点梳理
+## 数据清洗与模型训练进展
+- **数据清洗**：混合语料库数据清洗流水线完成第二轮，长尾噪音、极端口音和背景人声重叠片段单独分流，有效语音时长占比从89%提升至94%。
+- **标注对齐**：重新校对CTC的blank token分布，发现多音字和连读场景切分点偏，计划用新基准跑一轮消融。
+- **验证集表现**：数据质量提升后验证集WER下降约0.8个点；低资源语言混合边界场景下识别边界切分仍有毛刺，中英文切换时模型易吞掉过渡音或重复解码。
+- **架构调整**：计划将全纯Transformer架构换成流式RNN-T和Transformer混合形态，先在20小时核心数据上训练。
+- **数据增强**：已加时间偏移，但对背景白噪声和混响鲁棒性不足，准备引入MixUp和Cut再迭代一轮。
+## 推理延迟与动态Batching优化
+- **现状问题**：现有动态Batching在长短音频混排时首字延迟波动在150ms到300ms之间，产品反馈体验不连贯。
+- **优化方案**：改为静态分段加流式解码组合方案——音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码；目标首字延迟控制在80ms以内，整体吞吐量稳定在120路并发。
+- **VAD阈值**：暂定-25dB，结合能量和谱熵双模型判断；组长要求B做消融实验，画误切率和漏切率曲线找最优解，不能只盯延迟。
+- **线上验证**：下周拉线上流量回放做端到端对比，前后帧特征打点日志便于排查切分点对齐影响。
+- **显存评估**：RNN-T的prefix LM缓存拟做INT8量化配合动态缓存释放策略，预计压降30%左右显存占用；具体显存曲线和压测数据未跑完，明天下午发群里同步阈值。
+## 长音频解码卡死问题
+- **问题现象**：线上出现超长连续带方言口音音频，解码器陷入无效循环导致loop卡死，直接触发服务器节点重启。
+- **根因分析**：解码器默认max steps为2048个token、超时5秒，但部分音频解码序列长度超阈值且未做优雅降级，直接报OOM；RNN-T的attention权重一直震荡未收敛。
+- **修复方案**：加early stopping机制——连续30步置信度低于0.2时强制截断并返回当前序列，可解决90%以上卡死问题；同时完善超时熔断和降级返回。
+- **决策口径**：组长明确稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度。
+- **数据配比**：A训练时注意长序列数据配比，不能全塞短音频。
+## 监控面板与CI自动评估流水线
+- **监控需求**：现有日志系统无法落盘线上推理中间特征和中间帧，排查问题靠猜；计划接入Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标。
+- **告警分级**：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增；组长要求阈值设合理，避免半夜误报。
+- **CI评估流水线**：用GitLab CI跑自动评估——代码合入触发数据拉取、模型加载、测试集解码、结果对比，WER未下降或RTF超标直接打回。
+- **压测闭环**：B的推理服务压测脚本挂到流水线，输出标准JSON格式供直接读取。
+## 前端32k采样率升级
+- **问题**：前端SDK音频采样率16k，新模型输入32k，上采样会引入高频伪影影响识别率；32k模型在长尾词上WER比16k好0.5%。
+- **排期冲突**：前端对接人称排期推至下个月；组长计划拉产品和技术总监优先插队。
+- **备选方案**：服务端加实时重采样小模块做兼容，但会增加CPU开销；A建议先由B写轻量级重采样插件，用libresample实测CPU占用和延迟影响再决策，CPU开销控制在5%以内再提方案。
+## 结论与决定
+- **架构方向**：确认流式RNN-T混合架构和2秒切分方案，A和B分头推进，本周五前出详细设计和压测数据。
+- **稳定性优先**：长序列解码卡死问题先保稳定性、精度次之，下周先出热修复版本上灰度。
+- **算力协调**：下周一开始划拨三块A100做增量训练，需与NLP组错峰运行、看调度面板。
+- **双线保障**：流式架构切换不能影响现有非流式离线批处理，测试用例需覆盖全。
+## 行动项与分工
+- **A**：负责写CI评估脚本和流水线配置，周四前出V1版本；周三前把CI脚本和测试用例发群里评审。
+- **A**：负责长序列数据配比和边界用例验证，配合评估流水线对接。
+- **B**：负责改解码逻辑（early stopping、超时熔断、降级返回），周四提测热修复版本。
+- **B**：负责VAD阈值消融实验，画误切率和漏切率曲线；下周拉线上流量回放做端到端对比。
+- **B**：出监控指标定义文档，明天下班前发组长；出前端32k对比文档和重采样插件实测。
+- **组长**：拉产品和技术总监过前端32k升级事项，优先插队；转发监控指标文档给运维负责人。
+## 待确认与风险
+- **显存风险**：RNN-T的KV Cache显存峰值在并发量高时容易飙高，可能导致OOM；INT8量化压测数据未跑完，明天下午发群里确认阈值。
+- **VAD阈值**：-25dB在真实线上底噪环境下是否最优待线上回放验证；阈值设太高切掉轻声尾音致缺字，设太低增加无效推理。
+- **热词注入**：流式解码和静态切分的衔接是否影响热词注入的实时生效，待验证。
+- **重采样开销**：服务端重采样模块的CPU开销和延迟影响待B实测，CPU开销需控制在5%以内。
+- **算力冲突**：NLP组有四个job在排队，需错峰运行；A已调整启动脚本，优先跑验证集小的实验，大训练放周末夜间。</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3912/4028</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/now.xlsx
+++ b/now.xlsx
@@ -1,505 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h00984725\AppData\Roaming\WeLink_Desktop\appdata\IM\h00984725\DownloadFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE706B6-1704-48CA-BA2B-224A9DC5DE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞品对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指标统计" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="竞品对比" sheetId="1" r:id="rId1"/>
+    <sheet name="指标统计" sheetId="7" state="hidden" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0&quot;秒&quot;"/>
-  </numFmts>
-  <fonts count="5">
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="0"/>
-  <cols>
-    <col width="55.375" customWidth="1" style="5" min="1" max="1"/>
-    <col width="56.125" customWidth="1" style="5" min="2" max="2"/>
-    <col width="9" customWidth="1" style="4" min="3" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="9">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>场景</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>纪要</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>消耗时间</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>文本长度</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="13.5" customHeight="1" s="9">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:21
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="91">
+  <si>
+    <t>准确性</t>
+  </si>
+  <si>
+    <t>相关性</t>
+  </si>
+  <si>
+    <t>通顺性</t>
+  </si>
+  <si>
+    <t>其它问题</t>
+  </si>
+  <si>
+    <t>• 发言者 1 00:21
 最近呢霍伊斯根主席各位朋友，各位同事，我们所处的是一个更加变乱交织的世界。大家都关心这个世界今后向何处去。借用今年慕安会报告的主题来回答的话，那就是走向多极化。80年前联合国成立时，只有51个会员国，到今天是193个国家，共乘一艘大船。多极化的世界既是历史的必然，也正在成为现实。多极化是否会带来动荡失序，冲突对抗是否意味着大国主导弱肉强食。中国给出的答案是我们应当推动平等有序的世界多极化。这是习近平主席提出的又一个重大主张，也是我们对多极世界真诚的期许。中国必将是多极体系中的确定性因素。将坚定做变革世界中的建设性力量。在此我表达4点看法。一是应当倡导平等相待，列强争霸曾给人类带来灾难。两次世界大战殷鉴不远，殖民体系也罢，
 • 发言者 1 01:58
 中心外围体系也罢，不平等的秩序注定土崩瓦解。世界各国独立自主，风起云涌，国际关系民主法不可阻挡。坚持权利平等机会平等规则平等，应当成为建设多极世界的基本原则。正是秉+D5持这样的原则，中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。这不会导致西方的缺失，而将促进世界的正和慕安会近年来邀请更多全球南方国家出席会议，这是明智之举。每一个国家的声音都应该得到倾听。每一个国家都可以在多极格局中找到自身的位置，发挥自己的作用。二是应当尊重国际法治。中国有句古话没有规矩不成方圆，
@@ -557,74 +109,9 @@
 and IT would be very good that what you are,what you are also proposing. More talks and discussion on these issues withmaterialS here in munich. I wish you again. Good luck to you on your trip to new york and thank you for being such a goodguest here to the munich security conference.
 • 发言者 2 25:12
 Thank you for this all the best. .</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>新闻发布</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t># 王毅慕安会阐述平等有序世界多极化主张
-## 发布会概况
-本次对话系慕尼黑安全会议期间举行，中国外交部长王毅发表主旨演讲并接受主持人提问。王毅以慕安会报告主题"走向多极化"为引，指出多极化是历史必然，中国主张推动平等有序的世界多极化，并提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅强调，中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。随后，主持人就国际秩序与联合国改革、乌克兰危机、中美关系等议题提问，王毅逐一回应，重申中方维护以联合国为核心的国际体系、坚持劝和促谈、对美政策保持连续性与稳定性的原则立场，并介绍中方在乌克兰问题上的具体斡旋行动。
-## 核心信息
-### 多极化主张
-- 以慕安会报告主题"走向多极化"为引，指出多极化是历史必然，中国主张推动平等有序的世界多极化。
-- 提出四点看法作为建设多极世界的基本原则：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。
-- 明确中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。
-### 国际秩序与联合国改革
-- 中国是在现行国际秩序中发展起来的，是这一秩序的受益者，主张按照大多数国家愿望推动秩序向更加公正合理方向发展。
-- 各方应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是国际社会的最大公约数。
-- 联合国成立时51个会员国，今天已有193个国家。
-- 中国加入了几乎所有普遍性政府间国际组织和**600多项**国际公约，承担超过**20%**的联合国会费。
-- 中国切实履行巴黎协定，建成世界上最大的清洁发电体系。
-- 习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，以及构建人类命运共同体理念。
-### 乌克兰危机
-- 中俄是两大邻国，两国交往属正常国家间交往；中国需要巨量油气满足民众需求，将经贸问题政治化不可接受。
-- 中方主张一切争端和冲突应通过对话寻求政治解决，自危机爆发第二天（2022年2月25日）即提出对话协商解决。
-- 习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。
-- 中方派出特使斡旋，同巴西等南方国家发起"和平之友"。
-- 中方乐见美国同俄罗斯达成的共识，认为所有当事方和利益攸关方应适时参与和谈，欧洲更有必要为此发挥重要作用。
-### 中美关系
-- 中国对美政策保持连续性和稳定性，坚持相互尊重、和平共处、合作共赢三原则。
-- 中方愿按照三原则同美方构建稳定健康可持续的双边关系。
-- 若美方仍对中国打压遏制，中方必将奉陪到底，坚决回击美方单边霸凌行径，坚定维护中国主权、国家尊严和正当发展权利。
-## 官方表态
-### 多极化与国际秩序
-- **多极化是历史必然**：多极化是历史发展必然趋势，中国主张推动平等有序的世界多极化，倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。
-- **维护联合国核心地位**：各方应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是国际社会的最大公约数。
-- **推动秩序公正合理发展**：中国是现行国际秩序的受益者，主张按照大多数国家愿望推动秩序向更加公正合理方向发展。
-### 乌克兰危机
-- **坚持劝和促谈**：中方主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不能真正解决问题。
-- **反对经贸问题政治化**：针对主持人关于减少购买俄油气的建议，王毅反问称，若中国不从俄罗斯购买，没有哪个国家能提供如此巨量油气满足中国民众需求，"那是不可能的，也是不保险的"。
-- **支持和平进程**：中方乐见美国同俄罗斯达成的共识，认为所有当事方和利益攸关方应适时参与和谈，欧洲更有必要为此发挥重要作用。
-### 中美关系
-- **保持政策连续性**：中国对美政策保持连续性和稳定性，坚持相互尊重、和平共处、合作共赢三原则。
-- **坚定维护自身权益**：若美方仍对中国打压遏制，中方必将奉陪到底，坚决回击美方单边霸凌行径，坚定维护中国主权、国家尊严和正当发展权利。
-## Q&amp;A环节
-**主持人**：当前国际秩序受到质疑，俄罗斯入侵乌克兰、美国总统威胁使用武力等案例引发担忧，中国是否仍相信联合国及宪章？是否推动联合国改革？
-**王毅**：中国是在现行国际秩序中发展起来的，是这一秩序的受益者，主张推动秩序向更加公正合理方向发展。各方应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是国际社会的最大公约数。
-**主持人**：俄罗斯已成为"中国的加油站"，中国能否通过减少购买俄油气或停止双用物品贸易向俄施压？
-**王毅**：中俄是两大邻国，两国交往属正常国家间交往。中国需要巨量油气满足民众需求，若中国不从俄罗斯购买，没有哪个国家能提供如此巨量油气来满足中国民众的需求，"那是不可能的，也是不保险的"。将经贸问题政治化不可接受。中方在乌克兰问题上坚持劝和促谈，主张一切争端和冲突通过对话寻求政治解决。
-**主持人**：中美关系将如何发展？
-**王毅**：中国对美政策保持连续性和稳定性，坚持相互尊重、和平共处、合作共赢三原则，愿同美方构建稳定健康可持续的双边关系。若美方仍对中国打压遏制，中方必将奉陪到底，坚决回击美方单边霸凌行径，坚定维护中国主权、国家尊严和正当发展权利。</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>7004/2282</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="13.5" customHeight="1" s="9">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 01:35
+  </si>
+  <si>
+    <t>• 发言者 1 01:35
 好的，同学们欢迎回来。我们刚刚说了一点小小的插曲，但是没有关系，我们在接下来的时间里面呢，把时间交给咱们的电子科学与工程学院的三位老师，来给大家介绍一下我们学院的一个整体的情况。好。
 • 发言者 2 01:54
 同学们家长们上午好。首先我给大家汇报一下电子学院的学院历史情况。在电子科技大学建校之初，1956年就成立了无线电系，电真空器件系无线电零件系，1979年1992年2001年2018年，经过4次的院系调整，成立了电子科学与工程学院，科普示范性微电子学院。2023年响应国家新的号召，成立了电子科学与工程学院与基层电路学院。电子科学与与技术是电子学院的一级学科，它属于国家重点一级学科。它下面有5个二级学科方向，第1个是电磁场与微波技术，第二是电路与系统，第三是微电子学与固体电子学，第四是物理电子学。
@@ -774,75 +261,9 @@
 好，同学们后会有期了，再见。
 • 发言者 2 53:06
 好再见。</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>沟通交流会</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t># 电子科技大学电子科学与工程学院研究生招生宣讲会
-## 沟通背景
-电子科技大学电子科学与工程学院举办研究生招生宣讲会，由学院领导段院、柳教授、张教授、李天明教授及在读博士田雨桐面向考生和家长，系统介绍学院历史沿革、学科布局、师资力量、科研平台、人才培养成果及招生政策。学院源于1956年建校时设立的无线电系、电真空器件系、无线电零件系，历经四次院系调整，于2023年成立电子科学与工程学院与集成电路学院，拥有电子科学与技术国家重点一级学科及3个国防特色学科。宣讲会依次介绍学院整体情况、电子信息材料与元器件、电磁场与微波技术、电路与系统、物理电子学等方向，并由在读博士分享择校经验。整体沟通基调为全面展示学科实力与科研条件，吸引优秀生源报考。会议最后解答了考生关于夏令营时间的关切，明确夏令营计划今年举办、具体时间待定，相关信息将通过QQ群发布，并进行了抽奖互动。
-## 核心信息
-### 1. 学院整体情况
-- **历史沿革**：学院源于1956年建校时设立的无线电系、电真空器件系、无线电零件系，历经1979、1992、2001、2018年四次院系调整，2023年成立电子科学与工程学院与集成电路学院。
-- **学科布局**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。
-- **学生规模**：本科生现有1545人，招生专业为工科试验班（电子工程类）；研究生现有硕士和博士研究生1975人。
-- **师资队伍**：教师总数302人，含两院院士2人、领军人才19人、青年人才28人、其他类型人才12人、后备61人；拥有2个全国高校黄大年式教师团队，2022年获批4个国家自然科学基金创新群体。
-- **科研经费与成果**：近5年科研经费到账稳定在3~4亿元，以纵向项目为主；牵头获得国家科技奖励11项，近5年发表高水平学术论文2000余篇，申请专利1600余件、授权1300余件。
-- **科研平台**：拥有2个国家级平台、4个国际合作平台、7个省部级科研平台；科研团队20个，年度经费过千万元的团队15个，其中过亿元团队1个。
-### 2. 电子信息材料与元器件方向
-- **方向定位**：以电子在物质中的输运特性为基础，以材料为基础、器件为核心、应用为目标导向；2021年中国集成电路电子产品进口额度达2.8万亿元，约为原油进口量的1.7倍，属最紧迫的卡脖子问题之一。
-- **邓龙江院士团队**：现有研究人员19人，近年发表包括Nature在内的论文300余篇，承担课题130余项，年均到账经费3000多万元，获国家科技进步/技术发明二等奖共3项。
-- **张怀武教授团队**：现有研究人员17人，开展LTCC材料及集成技术、微波毫米波晶圆及器件等研究，承担项目100余项，发表SCI论文400余篇，年均到账经费2000余万元。
-- **平台条件**：依托2个国家级平台，科研面积2万余平米，建设两条国家重大任务试验生产线，拥有大型设备/系统500余台套；已获国家技术发明等奖项共计7项。
-- **人才培养**：毕业生去向包括英特尔、中芯国际、华为、德州仪器等企业；在读学生杨伟豪以第一作者在Nature Electronics、Nature Communications各发表一篇论文，5G滤波器芯片学生团队获挑战杯四川省金奖。
-### 3. 电磁场与微波技术、电路与系统方向
-- **学科概况**：电磁场与微波技术含4个细分方向，始于1956年建校时期，所属一级学科入选双一流A类学科；电路与系统学科1981年开始招收研究生，1988年成立首批博士后流动站。
-- **团队与成果**：电磁场与微波技术有6个团队；杨世文教授团队强耦合超宽带相控阵成果应用于中电14所某大型机载相控阵雷达，计算电磁学算法被评为20世纪十大算法之一。
-- **标志性成果**：樊勇教授团队成功研制0.22THz、0.34THz、0.42THz雷达成像系统，分辨率小于1厘米；太赫兹通信成果在2023年成都大运会田径项目示范应用。
-- **平台条件**：拥有国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室；硬件平台拥有中国高校最先进的微波暗室群体。
-- **人才培养**：连续三年获全国大学生集成电路创新创业大赛奖项；就业领域包括华为、中兴等领军企业及各大研究所、高校。
-### 4. 物理电子学方向
-- **学科定位**：物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学，产生新型电子器件；典型应用包括微波电子学（微波电真空器件）与光电子学（光电器件）。
-- **发展历程**：起源于1956年建校时成立的电子器件专业，1979年成立高能电子学研究所，2018年合并成立电子科学与工程学院；经过近70年发展，拥有自主知识产权商用软件MMST和切皮克。
-- **科研实力**：每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心；拥有3个四川省工程中心或重点实验室，2023年成功举办行业顶级会议。
-- **研究方向**：系统应用包括回旋行波管毫米波雷达、行波管无线输能系统、磁控管微波能干燥系统；横向拓展至毫米波、太赫兹频段及医学交叉领域。
-- **学生出口**：物理电子学方向共有9个团队，团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他。
-### 5. 学生视角分享与招生咨询
-- **择校理由**：成都为国家中心城市、新一线城市，电子信息产业发达；电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一；学院拥有四大学科和19个科研团队。
-- **团队情况**：田雨桐所在毫米波技术与系统应用团队负责人为樊勇老师，围绕微波毫米波理论与技术等五大方向开展研究，硕博毕业生实现100%就业率。
-- **奖助体系**：包括国家奖学金、学业奖学金、专项奖学金、新生奖学金、校园地国家助学贷款和生源地助学贷款等。
-- **择导师建议**：先选研究团队再选导师，可通过学院网站、IEEE Xplore和中国知网等检索导师论文和指导研究生情况。
-## 各方诉求
-- **学院领导段院**：全面展示学院历史沿革、学科实力与科研平台，明确学院2023年响应国家号召成立电子科学与工程学院与集成电路学院，突出国家重点一级学科与国防特色学科布局，吸引优秀生源报考。
-- **柳教授**：强调电子信息材料与元器件方向在解决国家卡脖子问题中的关键作用，以2021年集成电路电子产品进口额度2.8万亿元、约为原油进口量1.7倍的数据说明紧迫性，展示两大团队科研经费与成果实力。
-- **张教授**：突出电磁场与微波技术、电路与系统两个方向的学科历史积淀与应用成果，以双一流A类学科、20世纪十大算法、太赫兹雷达成像系统等标志性成果彰显学科竞争力。
-- **李天明教授**：强调物理电子学方向的基础性与前沿性，以每年近2亿元科研经费、国际最大真空器件研究中心、自主知识产权商用软件等展示方向实力，说明学生出口约1/3硕博连读、1/3去企业、1/3去研究所。
-- **田雨桐（在读博士）**：从学生视角分享选择电子学院的8个理由，包括成都产业优势、学科A+评级、团队100%就业率及完善奖助体系，建议考生先选研究团队再选导师。
-- **考生及家长**：关注夏令营举办时间，希望明确具体安排以便规划报考。
-## 沟通结果
-**达成共识**
-- **夏令营安排**：学院计划今年举办夏令营活动，具体时间待定，相关信息将通过QQ群（群号978499108）发布。
-- **抽奖互动**：直播抽奖口令确定为"一生一世逐梦未来"，奖品为学校马克杯套装。</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>112</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>13887/3230</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="13.5" customHeight="1" s="9">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:01
+  </si>
+  <si>
+    <t>• 发言者 1 00:01
 然后我再说一下我们这个议程，就是我会说个几分钟，就是我们这一年的一些发展状况，就主要是一些数据，就是你比如说营业额开票额，包括年终奖的总额，我们今年也公布一下，但是个人上我们就决定就不一一的公布了，这个我们也和大家去聊，包括我也和一些朋友去参考了一些东西。然后然后我反正我总结完之后呢，我们我会给就是每一个我因为我们现在也分了短视频，商务商务没有坐在一起，商务还有我们的无论你叫文案也好拍，摄也好，拍摄都算执行吧，
 • 发言者 1 00:43
 几个部门每个部门进行一个简单的一个评价，然后评价完之后我们就从这边开始好了，艺人就每个人都会就是说两句评价，但是一般都是肯定性的，有个问题性的，我们明年再说和去年大家应该也比较熟悉，我们就你可以理解为夸两句我们发个红包。然后我们评价完之后，然后那个就个人完评价完之后，我们就是在发这个就是我评价你的时候，你也可以逼几句就说几句，也可以没有台词，这个无所谓，如果但是说实话，人家有些公司特别是机构组织架构大的数值是非常重要的一个环节。
@@ -1362,87 +783,9 @@
 nice准备321起。
 • 发言者 1 01:18:10
 好勒。</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>总结复盘会</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t># 公司2023年度经营总结与年终颁奖会议纪要
-## 复盘概况
-2023年度公司经营总结与年终颁奖会议于年末召开，由老板主持，全体员工参加。会议预期目标为：总结年度经营状况、公布年终奖发放标准、对各部门员工进行评价与颁奖，增强团队凝聚力。实际达成方面，会议完整走完全部议程，年终奖总额确定为226,000元，个人数额不逐一公布；公司全年实打实支出390万元（含人员工资、外援配音、字幕、租机器），利润率约为24%或27%，成本控制较差；公司总量提升，但结余到账下滑，尚有百来万未收回；老板个人比去年少拿约10万元，公司亏损100万元。老板承认成本控制、人员招聘等管理问题，并明确明年开会再讨论成本控制。会议主线为：公布经营数据与年终奖标准，对短视频、执行、商务三个部门员工逐一评价，颁发最佳新人奖、最佳进步奖、后期独当一面奖、最佳员工奖、特别贡献奖五个单项奖，最后进行抽奖和聚餐安排。会议氛围轻松，老板多次强调对后期部门的侧重，并鼓励员工回应评价以促进跨部门了解。
-## 关键成果
-### 年度经营数据与年终奖发放
-- **年终奖总额**：确定为226,000元，个人数额不逐一公布；干满一年的员工从去年的4-5人增加到今年的12人。
-- **发放标准**：入职两三个月或半年以内的员工发红包，去年600-800元，今年约1000元；干满一年的员工以一个月基本工资为基准，表现好可更高；干满一年以上主要看年度表现，老员工且满意者预算可达大几万。
-- **薪酬概况**：最高工资（含年终奖）有2-3人达到20万元以上，平均工资到手1万多元；2023年人员工资支出比去年提高约25万元。
-### 短视频部门
-- **账号运营成果**：郭东辉负责所有平台运营，2023年实现粉丝显著增长——视频号从3月1日的70,019人增长到8万，小红书从1月的2000+增长到6.4万，抖音从2000+增长到5.7万，B站从3.1万增长到7.6万。
-- **涨粉拐点**：从6月20日第一条外拍对话视频开始有起色；此前潘老师曾10次提醒郭东辉出去找工作，项目差点放弃。
-- **变现进展**：账号变现程度满分10分达到7.05分；直播在视频号上直播4-5场，平均在线人数5000+，前100人平均在线50分钟以上。
-- **人员分工**：郭东辉负责所有平台运营，叶子负责剪辑和课程上架等琐事。
-- **红叶子评价**：入职两三个月（10月入职，11月转正），政委评价极高——既懂技术又懂英语，有把事情做好的精神头。
-### 执行部门
-- **刘腾宇**：评价最高，职业性、专业性、纪律性最好，迟到几乎没有，请假严格按规定，客户反馈好（宁波城市项目罗峰评价），年终奖在既定标准上因林海腾肯定再拉一档。
-- **欧阳**：刚满一年，有学习能力，技术进步明显，但沟通能力需提升。
-- **徐艺玲**：工作仔细认真，一遍过，技术有进步，从剪课程到剪宣传片。
-- **张文倩**：编导岗位，综合能力强，宁波项目完成出乎老板意料，但职场经验欠缺。
-- **市井**：后期技术标杆，最好的没有之一，期待能解决一些难题。
-- **钱德峰**：元老级，后半年拍摄密集，两个月连轴转无休息，还安排拍摄人员，期待更强执行能力。
-- **徐武安**：灵光，眼里有活，警察学院驻场辛苦，拍摄技术好于后期。
-- **宋俊逸**：编导，入职两三个月，第一个活宁波两分钟宣传片，效率高，文稿写得好，后续监狱、财经项目无问题。
-- **张扬**：公司邀请的人才，入职半年，职业态度和工作能力基本达到期待，老板认为2023年最有价值的事就是招他进来。
-- **李国宇**：满一年，拍摄水平较高，后期有灵性，但沟通能力需提升。
-### 部门整体评价
-- **短视频部门**：整体满意，认可克服困难的过程，期待明年账号开始变现，老板将投入更大精力。
-- **执行部门**：认可辛苦程度，今年项目没做砸过，期待老板更多组织协调，减少侵占休息时间。
-- **商务部门**：从结果看基本达到预期，实打实项目约300万元（老板估计），张扬认为不止。
-- **年终奖侧重**：老板明确年终奖侧重后期部门，后期比前期少一截，但拍摄的不会比后期少，这是老板唯一愿意解释的原因。
-### 颁奖与抽奖
-- **最佳新人奖**：颁给红叶子和张扬（各1人）。
-- **最佳进步奖**：颁给欧阳小元。
-- **后期独当一面奖**：颁给市井（政委搜名字，能完美胜任后期各种类型）。
-- **最佳员工奖**：颁给游腾宇（含金量最高，奖金稍多）。
-- **特别贡献奖**：颁给李海腾（奖金最多，运营层面重要）。
-- **证书与抽奖**：证书40元一本，皮质，字体认真对过；抽奖奖品包括一等奖充电宝（价值79元）、二等奖观影券（价值30元）、三等奖洗头膏（价值七八十元）、还有100元红包；老板让林彦腾发200元红包在群里。
-## 亮点事项
-- **短视频账号实现多平台突破性增长**：郭东辉负责运营，2023年视频号从70,019人增长到8万，小红书从2000+增长到6.4万，抖音从2000+增长到5.7万，B站从3.1万增长到7.6万。涨粉拐点出现在6月20日第一条外拍对话视频，此前项目差点放弃，最终克服困难实现突破，老板对短视频部门整体满意。
-- **直播互动数据表现突出**：视频号直播4-5场，平均在线人数5000+，前100人平均在线50分钟以上，为后续账号变现打下用户基础。
-- **执行部门全年项目零失误**：老板认可执行部门辛苦程度，今年项目没做砸过，客户反馈良好（如宁波城市项目获罗峰好评），刘腾宇获评职业性、专业性、纪律性最佳。
-- **关键人才引进见效**：张扬作为公司邀请的人才，入职半年职业态度和工作能力基本达到期待，老板认为2023年最有价值的事就是招他进来。
-- **后期部门整体进步明显**：林海腾（后期负责人）负责后期安排，今年后期整体进步大，分级模糊，效率提升；市井获评后期技术标杆，能完美胜任后期各种类型。
-## 不足事项
-- **成本控制差，利润率偏低**：公司全年实打实支出390万元（含人员工资、外援配音、字幕、租机器），利润率仅24%或27%，不可观；老板承认成本控制非常差，明确明年开会再讨论成本控制问题。
-- **公司亏损与到账下滑**：老板个人比去年少拿约10万元，公司亏损100万元；公司总量提升，但结余到账下滑，还有百来万未收回。
-- **人员不足导致加班频繁**：老板承认是判断失误，执行部门员工后半年拍摄密集（如钱德峰两个月连轴转无休息），期待老板更多组织协调，减少侵占休息时间。
-- **外援成本高**：部分因技术水平达不到而使用外援，有员工建议公司内部人员参与拍摄以减少外援成本——"其实有一些东西我们公司自己人内部就可以搞定了，比如说上午谁有空谁去一下，其实就是很简单的按个机位。"
-- **账号尚未充分变现**：变现程度满分10分仅达7.05分，直播尚无课程可变现，期待明年账号开始变现。
-- **部分员工沟通能力待提升**：欧阳、李国宇被指出沟通能力需提升；张文倩职场经验欠缺。
-## 改进计划
-- **成本控制专项讨论**：针对成本控制差、利润率仅24%或27%的问题，老板明确明年开会再讨论成本控制，需系统梳理人员工资、外援配音、字幕、租机器等支出项，制定降本举措。
-- **推进账号变现落地**：针对账号变现程度仅7.05分、直播尚无课程可变现的问题，由郭东辉继续推进账号变现与直播运营，协同叶子负责剪辑和课程上架等事务，老板将投入更大精力支持。
-- **优化人员配置与招聘**：针对人员不足导致加班频繁的问题，老板需反思招聘判断失误，补充关键岗位人员，减少对员工休息时间的侵占。
-- **减少外援依赖**：针对外援成本高的问题，评估内部人员参与拍摄的可行性（如简单按机位），同时鼓励李国宇等员工提升技术水平以减少外援使用。
-- **提升员工沟通能力**：针对欧阳、李国宇沟通能力需提升的问题，在后续项目中加强沟通训练与反馈。
-- **强化执行部门组织协调**：老板需更多组织协调，合理安排拍摄排期，避免两个月连轴转无休息的情况重演。</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>24562/3382</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="13.5" customHeight="1" s="9">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:10
+  </si>
+  <si>
+    <t>• 发言者 1 00:10
 装备了。调出来的时候我们生活
 • 发言者 2 00:17
 还让你上学或者不含不含那三个月工资。再加15%的就是15个群体。但是他那个比如是不是刚才说的就是流失额流转，所以去不上退的时候，快递他原来我们交的，那他不知从后边才来的，他都交费了。交费当时是什么呢？当时是我的公司管理工作。什么时候能达到10,200人，这块不能不太清楚其他的职业吧。能推进去。都可以。就退回去吧，我再推进点推，但是他出去他是上网的。从而选择一个地方可以。我们还有10多年的这个项目。
@@ -1968,73 +1311,9 @@
 你们再那个啥了。就是我和他
 • 发言者 2 01:03:16
 关系就是啥意思？</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议是小区业委会、业主代表与物业公司及办事处领导就小区物业服务问题召开的专项沟通协调会，由办事处主持，旨在坦诚沟通、化解对立。业委会成员提出，小区业主自发组织接龙，约200位业主参与，主要诉求是召开业主大会表决物业去留，并强调唯有业主大会具备此项表决权。业委会系统列举了小区自交房以来长期存在的10项突出问题，涵盖门柱灯、水系、监控、绿化、围墙、民生配套、雨水倒灌及人员配备等方面。物业经理逐一回应，称多数问题属地产前期配套遗留，非物业责任范围，并强调业主欠费高达170多万元、经营持续亏损，要求先回款40万元再实施维修。双方就服务与收费先后顺序激烈交锋，物业公司宣布将于本月起诉业委会，理由是阻碍经营、造成经济损失；业委会表示支持起诉并将提起反诉。办事处领导尝试调解未果，会议最终未达成任何共识，业委会决定按流程正常推进业主大会，双方同意走法律程序解决纠纷。
-## 要点梳理
-### 1. 会议开场与议题背景
-- 主持人强调会议目的是坦诚沟通、共同解决问题，避免对立情绪。
-- 业委会成员提出，业主自发组织接龙，约200位业主参与，主要诉求是召开业主大会表决物业去留。
-- 业委会强调，无论是业委会还是个别业主，均无权单方面决定撤换物业，唯有业主大会具备此项表决权。
-- 小区业主群组织情况：业委会工作组群唯一一个，准业主分5个群，共6个群；最早业主群由老邱哥建立，已有5、6年历史。
-### 2. 业主列举问题与物业回应
-- 业委会成员系统列举小区自交房以来长期存在的10项突出问题：
- - 入户庭院门柱灯从未开启。
- - 内部水系及售楼处迎宾水系从未运行。
- - 监控系统几乎全部损坏，上月小区进贼时警方未能从监控获取有效数据；监控室原配备24小时值班及一键呼叫功能，现已荒废且无人值守。
- - 绿化大量死亡且维护不力。
- - 北边围墙长期以烂铁皮遮挡，存在缺口，社会人员可随意进出，安全隐患突出。
- - 快递柜、直饮水机、宽带覆盖、暖气开通等民生配套长期无进展。
- - 雨水倒灌问题自2019年起持续存在，造成业主财产损失。
- - 物业人员配备严重不足，办公室人员由约10人减至4人，维修人员由5人减至2人。
-- 物业经理对业主列举的问题逐一回应，称多数问题属地产前期配套遗留，非物业责任范围：
- - 门柱灯因能耗成本过高未开启。
- - 水系存在严重质量问题，泵无法运转，应由地产维修。
- - 监控损坏因维修费用超出运营承担能力。
- - 绿化死亡因冬季无法更换。
- - 北边围墙位于红线以外且涉及违建，物业无处理权限。
- - 民生配套属地产前期配套。
- - 雨水倒灌属地产设计问题。
- - 人员配备不足因地产补亏款未结。
-- 物业经理强调，园区保护收入约100万元，人工成本超100万元，每年均处于亏损状态；业主欠费高达170多万元，要求先回款40万元再实施维修。
-### 3. 双方立场交锋与法律威胁
-- 业委会成员坚持物业服务无滞后性，全滨州小区均无先收费后服务的先例，要求物业先恢复正常服务，再讨论收费问题。
-- 物业经理坚持因业主欠费导致经营困难，无力改善服务，并宣布已与集团法务沟通，将于本月正式起诉业委会，理由是业委会成员在业主群煽动业主不缴费、阻碍正常经营、造成经济损失。
-- 物业经理称已与高级人民法院、滨城区人民法院沟通，有沟通记录，并掌握业主群内相关证据。
-- 业委会成员表示支持起诉，并将提起反诉。
-### 4. 调解尝试与最终僵局
-- 办事处领导尝试调解，建议物业拿出实际行动赢得业主信任，指出服务改善是业主缴费的前提，双方应互相体谅。
-- 双方分歧过大：物业经理坚持因欠费无法改善服务；业委会成员认为已无调解必要，决定推进业主大会表决。
-- 物业经理透露，地产公司已申请破产，无法追讨配套问题。
-- 会议最终未达成任何共识，双方决定走法律程序解决纠纷。
-## 结论与决定
-- **业委会决定正常推进业主大会**：按流程组织推进，表决议题为物业去留，并做好与全体业主的沟通与意见征集，确保程序合法合规。
-- **物业公司决定本月起诉业委会**：理由是阻碍经营、造成经济损失，将整理业主群内相关证据作为诉讼依据，于本月内向法院正式起诉。
-- **双方同意走法律程序解决纠纷**：办事处继续关注纠纷进展，协调双方保持沟通渠道，引导依法依规解决问题。</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>21511/1818</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="9">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 02:06
+  </si>
+  <si>
+    <t>• 发言者 1 02:06
 就是
 • 发言者 2 02:06
 都是一些比较基础的问题，因为我挑的这4个这个博士生，我自己代表这个多模态大模型和具身智能的这个融合这个方向。然后呢雄辉呢是这个于洋老师的博士生，他是这个强化学习做得非常厉害，然后呢薛寒博士呢是卢策武老师的博士生，然后呢他是在这个数据的这个收集以及这个柔性物体的操作方面非常的有心得，然后志龙呢也是于洋老师的博士生，他是在这个具身模型世界模型方面非常有建树，然后我非常期待志龙和这个赵昊老师能在这个世世界模型上能够有一些这个碰撞，就是其实是两个领域，因为志龙呢是从这个做强化学习那一套这个据世界模型来入手的。
@@ -2266,66 +1545,9 @@
 Exactly,然后被标准化以后，应该也对应该也没有什么大问题，最后技术上会是比较统一的，但是business上会是一个很加复杂的问题，因为他们赌的就是会脱钩会卡脖子嘛是吧？这就是另一个问题了。Ok好，我就大概简单说这么多。
 • 发言者 2 01:03:04
 好感，那感谢各位老师还有各位同学的这个精彩发言。然后看大家还有要补充的。要发言的吗？那那个没有的话，那感谢各位老师，然后那个那我们这次的那个圆桌论坛就结束了，也感谢各位听众来等一下。那各位老师我们合张影就是那个那感谢各位听众来。参加我们这个会议，相信今天这个我觉得今天整个从报告到这个圆桌论坛的质量，还是能匹配得上一个顶会的这个workshop的质量的，然后也希望大家能都值回票赞。</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>工作研讨会</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t># 具身智能与大模型融合技术路线圆桌研讨
-## 研讨概述
-本次圆桌论坛围绕具身智能与大模型融合展开，汇聚学术界与产业界专家，聚焦模型架构、硬件形态、世界模型、策略学习与数据策略等核心议题。与会者包括多模态大模型与具身智能融合方向代表、强化学习、数据收集与柔性物体操作、具身模型与世界模型等领域的博士生及产业嘉宾。会议旨在通过跨领域碰撞，厘清具身智能发展的关键技术路线与落地路径。讨论中观点交锋激烈，尤其在模型统一性、数据质量与仿真必要性上存在显著分歧，会议未形成统一结论，但明确了多个待探索方向。
-## 核心观点
-### 1. 模型架构与硬件形态
-- **端到端与分层之争**：发言者5认为模型不应从上到下完全端到端，而应至少分为大脑与小脑两层，大脑在硬件变化时无需重新训练，小脑应自适应肢体变化，并以断手后大脑仍能指导动作的类比说明分层必要性。发言者6从AI发展历程分析，认为当前多模态大模型微调并非终极方案，世界模型可能更接近人类水平，但亦非最终形态。
-- **人形与特种形态**：发言者5从机械与传感器角度质疑具身形态的收敛方向，提出机械智能概念，强调软手等硬件在抓取中的顺应性与摩擦优势。发言者4指出硬件可靠性与寿命是规模化评估的关键，现有工业机械臂并非为具身智能实验设计，需个人柔顺硬件结构支撑大规模评估。发言者6认为人形机器人因现实环境为人设计而必然存在，特种机器人在车厂与微电子制造厂已实现97%以上自动化，两类形态将长期共存。
-- **软硬件协同优化**：发言者2主张具身智能是软硬件协同优化的范式，以松龄产品两代迭代为例，说明第二代在遥操与策略部署上优于第一代，并提及凝胶夹爪在触觉反馈与摩擦力上的改进。
-- **产业投资视角**：发言者7预测具身智能将经历四波融资与形态变革，当前10亿级融资规模尚小，未来技术突破将深刻改变硬件与云端模型形态。
-### 2. 世界模型定义与作用
-- **强化学习视角**：发言者8定义世界模型为可交互的黑盒，追溯至1990-1991年Sutton的Dyna-Q文章，并指出2018年Schmidhuber与LeCun定义世界模型包含表征与转移两个组件，强调可交互是强化学习世界模型的第一要义，当前世界模型在物理规律体现上欠缺明显。
-- **CV视角**：发言者7强调世界模型用于动态重建物理世界，可作为RL世界模型的工具，但当前三维视觉技术栈深、学术界RL领域较少关注三维表征。
-- **3D归纳偏置之争**：发言者7提出数据量决定是否需要3D归纳偏置，认为大规模数据下inductive bias需求减少，并以ImageNet、GPT成功为例，同时指出UniSim等近期工作仍需3D归纳偏置，预测未来数据规模化后更端到端方式更优。
-- **统一性分歧**：发言者5以游戏与物理世界跳楼场景为例，指出世界模型可能面临歧义问题，难以同时建模不同物理结构的dynamics，但policy可通过长观测窗口适应，因此世界模型可能无法统一，而policy可能统一。发言者9提出反对意见，认为不同物理结构可能有统一表征，可通过condition区分，但发言者5认为将M个独立世界模型装入高维可控模型在工程上更复杂，M个独立模型更简单。
-### 3. 强化学习与模仿学习路线
-- **模型强化加机理融合**：发言者10介绍公司采用模型强化加机理融合方式，指出监督学习数据分布不足以覆盖高维动作空间，强化学习强依赖仿真环境且sim-to-real迁移困难，融合方式更实际，并分享在强化学习任务分层中，上层决策用强化学习、底层执行用MPC或DWA等传统方法的实践经验。
-- **先模仿后强化**：发言者9主张复杂任务应先模仿后强化，单独模仿或强化均不可行，以AlphaStar、GPT为例说明强化学习从零训练样本复杂度不可接受，模仿提供先验信息无坏处，且当人类行为非最优解时需强化优化至超人类水平。
-- **反馈的重要性**：发言者5强调反馈在控制中的重要性，指出PID系统必有反馈，可将其作为强化学习的reward来源，支撑强化学习在真机上的可行性。
-- **两者并不冲突**：发言者11认为强化学习与模仿学习并不冲突，二者本质是获取运动先验的两种途径，有数据可用模仿学习，无数据可用强化学习生成，最终通过RL在隐空间完成任务。
-### 4. 数据采集与仿真数据策略
-- **数据质量把控**：发言者11强调视角与标定对数据质量的影响，指出Open X数据集融合多家数据但相机视角不固定，影响policy表现，其团队在采集时严格控制视角与标定，并记录物体运动信息，以提升数据质量。
-- **真实数据主张**：发言者4认为柔性物体仿真需先进图形学技术（如IPC），算力要求高且进展缓慢，真实数据是低成本方案，并指出互联网数据与机器人所需数据不匹配，如叠衣服视频多为平整状态，缺乏从混乱状态展平的常见任务数据，提出终极形态是脑机接口或机电式无感采集，现阶段可穿戴设备是可行方案。
-- **仿真与真实结合**：发言者2分享实验表明300条仿真数据加20条真机数据可显著提升成功率，并指出仿真数据可提供海量随机初始状态，弥补真机数据采集成本高的不足。
-- **无标注数据第三域**：发言者7提出加入无标注真实数据作为第三域，预测2025年将大规模利用无标注数据，并指出真实数据与仿真数据的选择应case by case看成本，同时提及国产仿真系统面临卡脖子风险，已有企业（如宋应）布局国产替代。
-## 研讨方案
-- **软硬件协同优化**：会议主要达成共识，具身智能需软硬件协同优化，硬件可靠性与寿命是规模化评估的关键前提。
-- **先模仿后强化**：发言者9主张复杂任务应先模仿后强化，单独模仿或强化均不可行，模仿提供先验信息，强化优化至超人类水平。
-- **无标注数据推广**：发言者7认为2025年应推广无标注真实数据的使用，作为真实数据与仿真数据之外的第三域。
-- **模型强化加机理融合**：发言者10公司采用模型强化加机理融合方式，上层决策用强化学习、底层执行用MPC或DWA等传统方法，作为产业落地的实际路径。
-- **仿真与真实数据结合**：发言者2实验表明300条仿真数据加20条真机数据可显著提升成功率，仿真数据提供海量随机初始状态，弥补真机数据采集成本高的不足。
-## 未决后续
-- **模型形态未定**：具身智能最终模型形态是端到端还是分层，大脑与小脑分离的可行性需进一步论证，发言者5需探索policy通过长观测窗口适应不同物理结构的方案。
-- **3D归纳偏置待验证**：世界模型是否需要3D归纳偏置，数据规模化后是否更端到端方式更优，需结合CV与RL两派观点深入碰撞验证。
-- **策略学习结合路径**：强化学习与模仿学习如何结合，需在任务分层设计中验证监督学习与强化学习结合的实际性能，发言者10负责落地优化。
-- **数据策略选择**：数据采集是真实数据还是仿真数据，需case by case看成本，发言者7推动无标注数据研究，发言者4推进可穿戴设备数据采集方案，并关注柔性物体仿真技术进展。
-- **生态依赖风险**：中国是否依赖英伟达生态，国产仿真系统面临卡脖子风险，需评估国产替代方案，已有企业（如宋应）布局国产替代。</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>21458/3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="13.5" customHeight="1" s="9">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:10
+  </si>
+  <si>
+    <t>• 发言者 1 00:10
 现在
 • 发言者 2 00:10
 公布法庭纪律在合议庭评判请诉讼各方参与人全体航行人员起立。你是对法庭的尊重。二诉讼各方参与人与全体旁听人服从法庭的指挥，尊重执法礼仪。遵守法庭纪律，不得实施下列一鼓掌喧哗。二吸烟禁食。三拨打或接听电话。四对庭审活动进行录音录像拍照或使用移动通信工具的传播途径活动。五其他危害。秩序的成为。三注重参与人发言或提问。应当经达成许可。是旁听人员不得进入审判活动区，不得随意站立走动，不得发言评论和记录。五在执行过程中，诉讼参与人或者旁听人员扰乱法庭秩序，情节较轻的，审判长可以口头警告制止训诫等。
@@ -2807,67 +2029,9 @@
 金融债权已得到充分保护。通过本案的审理，我们还发现本案设计的生产设备等动产抵押权与融资租赁物所有权的冲突，是司法实践中的普遍性的难题。金融风险防控还有较大的空间，其根本的原因是我们国家还未建立统一的动产登记制度，现有的动产融资租赁登记系统和动产抵押登记系统尚缺乏有效的衔接。未从根本上防范和解决此类矛盾纠纷。我们将根据最高人民法院关于加强司法建议工作的意见的规定，向有关部门提出司法建议。共同推进国家治理的现代化。
 • 发言者 3 01:48:18
 今天的庭审到此结束。阅看庭审笔录并签名。如有遗漏和差错可以申请补正。现在闭庭。</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>庭审记录</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t># 国开行与东源系企业金融借款合同纠纷二审调解结案
-## 庭审概况
-本案系国家开发银行（以下简称国开行）与云南东源电力股份有限公司（以下简称东源煤电）、云南东源曲靖电力有限公司（以下简称东源曲靖电力）、招银金融租赁有限公司（以下简称招银租赁）金融借款合同纠纷二审案件，由最高人民法院组成合议庭公开开庭审理。合议庭由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。国开行委托北京德恒昆明律师事务所邓劲松、刘双俊律师出庭，东源煤电、东源煤业、东源曲靖电力共同委托云南勤业律师事务所吴学成律师及东源煤业员工李新海出庭，招银租赁委托员工万海龙及上海盈泰律师事务所陈志超律师出庭。庭审围绕三个争议焦点展开：国开行对案涉设备是否构成善意取得抵押权、借款罚息复利计算及起算日期、东源煤电及东源煤业是否应连带给付违约金。经法庭调查、辩论及调解，各方最终达成调解协议，合议庭当庭予以确认。
-## 诉辩意见
-**国开行（上诉人）**：主张其对案涉设备构成善意取得抵押权，罚息复利计算有合同依据，东源煤电、东源煤业应连带给付违约金。
-- 国开行作为金融机构尽职调查有限，仅需针对抵押人东源曲靖电力公司调查，审查义务不能任意扩大至东源煤电。
-- 案涉设备为通用设备，无唯一标识码，无法特定化；已按人民银行规定查询融资租赁登记系统，未查询到登记记录。
-- 借款合同第6条第4款明确约定对不能按期支付的逾期借款利息按罚息利率计收复利，且不违反法律强制性规定。
-- 东源煤电未提起上诉，一审判决已支持罚息复利，依不告不理原则应予维持。
-- 借款合同第24条第3项约定违约金为千分之一，东源煤电未配合办理账户管理及柜台前移手续，构成违约，违约金金额未超过法定最高标准。
-**东源煤电（被上诉人）**：主张国开行未尽注意义务不构成善意取得，罚息不应作为复利计算基数，国开行未举证证明违约行为。
-- 东源煤电于2015年12月2日通过邮件向国开行发送《东源公司融资情况统计表》，其中招银租赁抵押物为恩洪电厂设备资产且已登记，国开行抵押物为恩洪电厂设备及在建工程，两者设备名称完全一致，且邮件中以红色标注，国开行作为专业金融机构应进一步核查。
-- 借款合同第24条第2款第2项约定宣布贷款提前到期需限期偿还，而非立即偿还，国开行要求当日全额偿还8.37亿元本金未给合理期限，有违公平原则。
-- 根据《人民币利率管理规定》第21条，仅对贷款期内不能按期支付的利息计收复利，未包括罚息；合同第6条第4款亦未明确罚息计收复利；最高人民法院2015年、2016年民事判决支持罚息不作为复利基数。
-- 国开行未举证证明东源煤电存在违约行为，且未按合同约定先行发出限期纠正的书面函件，举证不能的后果应由国开行自行承担。
-**招银租赁（被上诉人）**：主张国开行未在抵押时点查询融资租赁登记，不构成善意取得。
-- 根据人民银行规定，国开行应在抵押时点（2015年12月）查询融资租赁登记，但国开行仅提供2018年9月的查询记录，不符合要求。
-- 国开行审查义务应扩展至东源煤电，因其为借款人及抵押人全资控股母公司。
-- 融资租赁登记系行业指导性规范，不产生物权效力，但可强化权利外观；案涉5套设备为种类物，无唯一识别码，登记时未填写设备唯一标识码。
-- 融资租赁司法解释第9条第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
-## 举证质证
-- **融资情况告知邮件**：东源煤电出示2015年12月2日邮件及《东源公司融资情况统计表》，证明已向国开行告知招银租赁抵押物为恩洪电厂设备资产且已登记，国开行抵押物为恩洪电厂设备及在建工程，两者设备名称一致并以红色标注；国开行质证认为其审查义务仅限于抵押人东源曲靖电力公司。
-- **融资租赁登记查询记录**：国开行出示融资租赁登记系统查询记录，证明其以曲靖电力公司为查询对象未查询到登记记录；招银租赁质证认为国开行仅提供2018年9月查询记录，未在抵押时点（2015年12月）查询，不符合人民银行规定。
-- **回租设备清单**：招银租赁出示回租设备清单，载明设备出厂日期为2012年3月1日；国开行质证称其现场调查设备铭牌生产日期在2013年11月至2014年3月之间，两者存在矛盾。
-- **审计报告**：招银租赁出示一审证据第82页、95页审计报告，载明曲靖电力公司注册资本4亿元且已实缴；国开行未提出实质异议。
-- **借款合同及还款函**：国开行出示借款合同及2018年6月13日偿还贷款本金函，证明罚息自该日起算、复利计算有合同依据；东源煤电质证认为合同第24条第2款第2项约定需限期偿还而非立即偿还，且合同未明确罚息计收复利。
-- **设备抵押登记情况**：法庭核查国开行对93项设备享有抵押权、招银租赁对6项设备享有所有权的事实，双方对案涉全部发电设备整体盘活处置方案无异议。
-## 庭审结果
-**调解协议达成**：合议庭休庭评议后提出调解方案，各方均无异议，合议庭当庭予以确认并出具调解书。
-- 国开行对东源煤电债权扣除破产已清偿本金后，利息、罚息、复利合计6474.4513万元。
-- 招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元。
-- 国开行对93项设备有抵押权，招银租赁对6项设备有所有权，双方对案涉全部发电设备整体盘活处置，变现价款各得50%，费用各担50%。
-- 调解书生效后20日内，国开行向一审法院提出执行申请启动司法处置程序。
-- 若司法变现不能，双方放弃案涉设备权益，由东源曲靖电力自主生产经营。
-- 案涉设备管理费用由东源曲靖电力承担。
-- 一审诉讼费用中，国开行诉请部分按一审判决执行，招银租赁诉请部分由国开行承担；二审诉讼费用由国开行和东源煤电各承担50%。
-**程序安排**：审判长指出，本案系高质量调解，有助于云南煤化工集团、东源煤业、东源煤电破产重整圆满收官，企业重生并良性发展，金融债权得到充分保护。本案暴露的动产抵押权与融资租赁物所有权冲突系司法实践普遍性难题，根本原因在于国家未建立统一动产登记制度，现有融资租赁登记系统和动产抵押登记系统缺乏有效衔接，合议庭将依据最高人民法院关于加强司法建议工作的意见，向有关部门提出司法建议，共同推进国家治理现代化。</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>28485/2599</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="13.5" customHeight="1" s="9">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:11
+  </si>
+  <si>
+    <t>• 发言者 1 00:11
 我们可以开始了吗？可以了。好的，那我们开始开会。尊敬的合作局金昌柱以及公司国内的领导，那么根据我们验收工作安排，我们现在召开我们原占比二玉米面加工厂项目的中期验收会议。由于时间关系和工作安排，那个我们在昨天与那个合作局和金昌处的对接过程中，考虑到今天会议的时间的确定呢，以及这个有限的会议时间，我们提前召开了这个我们验收组以及参与单位的一个预备会，把截止目前完成的工作的情况呢，也做了一个梳理和内部通报，以期呢为这个参建单位提前争争取整改和完善的时间。
 • 发言者 1 01:08
 那么根据我们之前的计划和安排，由我来代表这个一会呢由我来代表验收组吧，截止目前工作的开展情况和存在的问题做一个简单的汇报和评述。然后呢请我们的管理组以及技术组就存在问题的逐渐整改情况做简单的做一个汇报。那么会后呢后面呢再请我们有关的领导做指示，那么会后呢继续安排我们剩下的一个点的这个现场验收工作。那么截止今天为止呢，我们以这个已经完成了卢萨卡点除弹料加工调试以外的所有唉验收工作。蒙蒙泽这个点呢已经完成了，
@@ -3007,65 +2171,9 @@
 好的好的，大家保重
 • 发言者 6 44:08
 唉行。</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>项目进度会</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t># 原占比二玉米面加工厂项目中期验收会议纪要
-## 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组组长王总主持。验收组于18号、19号提前介入项目前期摸排，20号召开首次会议。截至目前，卢萨卡点除带料加工调试外已完成所有验收工作，蒙泽点已完成全部验收工作并顺带进行了带料调试和试生产，某皮卡点的内业资料已提前拿到卢萨卡点。内业检查方面，项目执行团队基本能保证人员在前方岗位，内业资料基本满足项目有关标准和规范要求，竣工文件已达到基本组卷和成册要求，但需进一步分类整理和规范签字。外业检查方面，建筑、安装、机电设备三个板块总体质量良好，工艺设备运行正常，产能符合设计指标。验收组提出人员履约、内业资料、现场实体三个方面的整改要求，管理组和技术组分别表态将按要求整改。合作局金昌柱领导、公司林总先后发言，强调重视混凝土路面开裂问题、完善资料闭环、做好成品保护及注意交通安全。会议还补充了不可预见费使用问题，并安排后续工作。
-## 进度追踪
-| 模块 | 进展 | 状态 |
-| --- | --- | --- |
-| 卢萨卡点验收 | 除带料加工调试外已完成所有验收工作 | 进行中 |
-| 蒙泽点验收 | 已完成全部验收工作，顺带完成带料调试和试生产 | 已完成 |
-| 某皮卡点验收 | 内业资料已提前拿到卢萨卡点，现场验收待会后安排 | 未开始 |
-| 内业资料检查 | 基本满足项目标准和规范要求，竣工文件达到基本组卷和成册要求，需进一步分类整理和规范签字 | 进行中 |
-| 建筑部分外业检查 | 主要材料从国内采购或从卢萨卡集中采购，内在品质和外观质量达到良好标准 | 已完成 |
-| 安装部分外业检查 | 钢结构材料从国内定制发货，施工工艺和外观质量满足规范要求 | 已完成 |
-| 设备部分外业检查 | 设备参照中国标准定制，厂家高峰期派十几名人员现场指导安装，蒙泽点全流程生产调试仍在进行，工艺设备运行正常，产能符合设计指标 | 进行中 |
-| 人员履约检查 | 项目执行团队基本能保证人员在前方岗位，需完善个别人员进出场时间、护照及特种人员证件有效期问题 | 进行中 |
-## 风险预警
-| 风险卡点 | 影响范围 | 责任方 | 应对举措 |
-| --- | --- | --- | --- |
-| 混凝土路面开裂问题若未彻底解决，移交外方后可能出现大面积开裂 | 蒙泽厂区，对外影响 | 管理组、总包单位 | 共同研究制定科学合理的整改方案，在出报告前完成整改，验收组复核 |
-| 某皮卡点路途遥远且路况不好，验收组前往存在交通安全风险 | 验收组出行安全 | 验收组 | 注意交通安全 |
-| 赞比亚雨季来临，厂区排水系统可能存在阻塞风险 | 厂区排水系统 | 待对齐 | 列入现场实体整改项，需对排水问题整改 |
-| 设备监控管线接头脱落可能引起机械故障 | 设备运行安全 | 待对齐 | 列入现场实体整改项，需整改 |
-| 廊桥竖条数量不足，存在安全隐患 | 廊桥结构安全 | 待对齐 | 列入现场实体整改项，需加密整改 |
-| 不可预见费使用的具体证据和资料不完善 | 费用合规性 | 验收组 | 继续跟踪使用情况，完善依据证据和数据 |
-## 后续计划
-### 整改落实
-- **细化问题并制定方案**：管理组田组长会后与技术组细化验收组提出的问题，制定处理方案并逐一落实。
-- **人员履约资料收集**：技术组龚总负责收集人员履约资料，完善个别人员进出场时间、护照及特种人员证件有效期问题。
-- **现场实体整改**：技术组按方案对局部损伤、排水、混凝土路面裂纹、监控管线接头脱落、廊桥竖条加密等问题逐一整改。
-- **混凝土路面开裂整改**：管理组和总包单位共同研究制定科学合理的整改方案，在出报告前完成整改，验收组需复核。
-### 资料汇总
-- **三个厂区资料汇总**：技术组在验收完成后第一时间将三个厂区资料（含竣工图）全部汇总至卢萨卡，进行分类汇总、组卷及编码，严格按援外项目执行手册执行。
-### 验收后续安排
-- **某皮卡点现场验收**：会后验收组安排某皮卡点的现场验收工作，前往途中注意交通安全。
-- **不可预见费跟踪**：验收组继续跟踪不可预见费使用情况，完善相关依据证据和数据。
-- **成品保护**：做好成品保护，及时修补破损。</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>11110/1816</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="13.5" customHeight="1" s="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:02
+  </si>
+  <si>
+    <t>• 发言者 1 00:02
 各位尊敬的投资者，各位客户朋友们，大家周一早上好，欢迎来参加我们的每周一度的中金宏观策略争论，我是策略组的刘刚凯文。那我们今天呢也是带来了最近大家比较关心的一些热点内容，也是比较丰富的内容。首先呢这个关于这个大美丽法案是最近海外市场大家关注的焦点，他对美国经济对于美股市场美债有什么影响，对于美元流动性有什么冲击？那反过来呢是否会通过这个来影响港股的流动性，会影响呢外围资金流向的变化。这一点呢是我们今天给大家重点解读的一部分。
 • 发言者 1 00:38
 第2块呢大家可能也注意到了，就是那它到底有什么影响？那市场好像还反映的出奇的冷静。再加上呢这个市场也处在这个位置，也在观望接下来关税的谈判，所以在关税上我们给大家做一个更新。那除了这个以外呢，回到这个中国市场回到国内的基本面的情况，最近大家最为关心的政策上的变化呢就是所谓的反内卷。但反内卷对于不同行业的含义以及这一次呢可能的影响，我们呢请到了我们公用事业风光公用事业的首席分析师刘佳妮来跟我们谈谈对于行业层面的影响。
@@ -3259,96 +2367,9 @@
 好的，非常感谢雪晴老师给我们带来关于游戏行业的分享和更新观点，也是非常明确。接下来等待一定的催化剂，在目前的位置上呢依然是一个好的配置的时间点。而且呢有可能会迎来一定催化剂下，包括新品催化下的这个戴维斯双击。我们从策略角度呢也提示大家关注相关的板块。就像我刚才提到的一样，从这个大的方向上，我们去在合适的位置对吧？合适的这个位置上，合适的时间上去选择长期正确的板块，可能在结构性的行情下是更加符合现在策略的一个投资方向。
 • 发言者 1 01:12:37
 好，再次感谢那各位投资者如果有问题的话，可以直接联系这个传媒组和我们的雪琴老师。以上呢就是我们今天这一期宏观策略争论的所有的内容。内容还是非常丰富的，也是再次感谢各位投资者对我们持续的关注。我们下周同一时间再见，感谢大家。</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>新闻发布</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t># 中金宏观策略争论：聚焦海外热点与国内产业投资主线
-## 发布会概况
-本次中金宏观策略争论会议围绕海外市场热点与国内产业投资机会展开，策略组分析师刘刚凯文、公用事业风光首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就大美丽法案、关税政策与港股流动性、光伏反内卷政策、人形机器人及游戏板块等议题进行解读。会议整体强调在结构性行情中，于合适位置提前布局长期正确板块，关注创新药、人形机器人、AI应用等方向的配置机会。海外方面，大美丽法案对经济有正面作用但三季度存在流动性抽水效应，关税有效税率维持10-12%即可满足收入需求，港股基本面可盖过流动性边际收紧影响。国内方面，光伏反内卷政策力度升级至中央层面，硅料环节最易整合；人形机器人三季度关注华为云生态、本土企业技术闭环、特斯拉硬件替代三条主线；游戏板块调整后有望戴维斯双击。后续工作安排上，各分析师将持续跟踪政策落地细节、价格走势与新品表现，及时向投资者提示催化剂信号。
-## 核心信息
-### 大美丽法案与美股美债影响
-- 市场存在两大认知误区：将美元走弱等同于去美元化、将美元弱与美股弱直接划等号，不应以长期逻辑影响短期配置
-- 基于信用周期框架分析，美国经济环比有望改善，中国面临高基数压力
-- 大美丽法案三大块：提高债务上限**5万亿美元**、延长减税（新增支出**3.4万亿美元**，每年**3400亿**）、取消899条款
-- 关税收入每年**3000-4000亿美元**可覆盖新增支出，赤字率维持在**5-6%**
-- 三季度美债供给约**1万亿美元**，美债利率可能上行但幅度不及2023年（当时从**3.8%升至5%**，美股下跌**4-5%**）
-- 期限溢价已处于**2013年以来高位**，波动提供再配置机会
-### 关税政策与港股流动性
-- 关税四点信息：必须做、维持一定税率、不能太高、市场脱敏
-- 新变化：时间拖后、税率相对4月2日回落、对加拿大墨西哥欧盟单独处理
-- 当前有效税率测算**10-12%**，极端情况**18%**；对华关税约**40-50%**，越南转口限制**40%**
-- 需关注**8月1日**关税节点及**8月12日**中美谈判
-- 港股三季度美元流动性边际收紧，但基本面可盖过影响；金管局投放流动性使港币汇率处于**7.84-7.85**，港股点位**23000-24000**
-### 光伏反内卷政策与行业供需
-- 供需失衡背景：全球光伏装机从2020年**130GW**增至2024年**530GW**，2025-26年需求增速回落至**10%**左右；2023年产能从**600GW**增至**1000GW**
-- 产能过剩格局：电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**，产业链价格下跌**70-90%**
-- 反内卷政策从2024年行业协会主导升级到2025年中央层面（国常会、人民日报、中财委会议、工信部座谈会）
-- 硅料环节最易整合：现金成本**38元/公斤**，颗粒硅**28元**，尾部**45元**，多晶硅期货触及**40元/公斤**
-- 电池片供需最好，光伏玻璃需出清**2万吨**，BC渗透率**5-6%**
-- 价格信号初现：硅片报价涨**10%**，电池涨**2分钱**
-### 人形机器人三季度展望
-- 二季度板块回调：A股机器人板块跌**9%**，跑输机械**12个百分点**，特斯拉供应商股价回调**30-40%**，原因包括特斯拉量产延期和关税
-- 主线一：华为云生态开放——发布盘古世界模型和cloud robot平台
-- 主线二：本土企业技术闭环——智元机器人拟借壳上市，宇树科技年收入突破**10亿**，智元、宇树中标中国移动**1.2亿**采购订单
-- 主线三：特斯拉延期带来的硬件替代窗口——optimus存在电机过热、灵巧手负载不足、续航问题
-- 建议关注三类信号：华为云接入厂商、头部企业出货量、电机硬件优化
-### 游戏板块政策与新品周期
-- 政策友好度提升、版号发放常态化：6月发放**158个**（国产147+进口11），**2018年以来单月最高**
-- 市场规模增长：1-5月同比增长**17%**，手游同比增长**20%**
-- 新品表现：吉比特《仗剑传说》首月流水**2亿多**，巨人网络《超自然行动组》6月流水**过亿**
-- 估值仍有空间：A股游戏TTM PE约**30倍**（2023年AI行情**45倍**），2025年静态PE约**20倍**
-- 调整后有望戴维斯双击，建议关注明年业绩确定性
-## 官方表态
-### 大美丽法案与去美元化
-- **不认同去美元化共识**：美元弱不等于去美元化，美元走弱可有多种原因，如美联储降息预期升温均可导致美元相对走弱；不应以长期逻辑影响短期配置
-- **法案财政影响可控**：大美丽法案一年新增支出3400亿，可被关税带来的收入（每年3000-4000亿美元）弥补，赤字率不会大幅上升，维持在5-6%
-- **三季度流动性有压力但可控**：美债供给约1万亿美元带来抽水效应，美债利率可能上行，但幅度不及2023年三季度（从3.8%升至5%）
-### 关税政策
-- **关税必须做但税率不能太高**：维持一定税率即可满足收入需求，有效税率10-12%为可行区间，过高不可行
-- **市场对关税已脱敏**：关税时间拖后、税率相对4月2日回落、对加拿大墨西哥欧盟单独处理，市场反应趋于钝化
-### 光伏反内卷政策
-- **政府干预有必要**：光伏行业供需严重失衡、价格战持续、企业退出不足，在此位置期待政府干预，认为有一定必要性
-- **反内卷政策力度升级**：从2024年行业协会主导升级到2025年中央层面，政策有望夯实行业底部
-### 港股流动性
-- **基本面可盖过流动性影响**：三季度美元流动性边际收紧，但港股基本面可盖过影响，金管局投放流动性维持汇市稳定
-### 人形机器人
-- **三季度三大主线明确**：华为云生态开放、本土企业技术闭环、特斯拉延期带来的硬件替代窗口，建议关注三类催化剂信号
-### 游戏板块
-- **调整后有望戴维斯双击**：政策友好度提升、版号发放常态化、新品周期启动，当前估值仍有空间，建议关注明年业绩确定性
-## Q&amp;A环节
-**问**：大美丽法案对美债利率的影响幅度如何判断？
-**答**：三季度美债供给约1万亿美元，存在流动性抽水效应，美债利率可能上行，但幅度不及2023年三季度（当时从3.8%升至5%，美股下跌4-5%）。当前期限溢价已处于2013年以来高位，波动提供再配置机会。
-**问**：关税有效税率维持在什么水平较为合理？
-**答**：当前有效税率测算10-12%，极端情况18%。关税收入每年3000-4000亿美元，可覆盖大美丽法案每年3400亿新增支出，维持10-12%即可满足收入需求，过高不可行。
-**问**：港股三季度流动性收紧是否会影响港股表现？
-**答**：三季度美元流动性边际收紧，但港股基本面可盖过影响。金管局投放流动性使港币汇率处于7.84-7.85，港股点位23000-24000。需关注8月1日关税节点及8月12日中美谈判。
-**问**：光伏反内卷政策下哪些环节最值得关注？
-**答**：硅料环节最易整合（现金成本38元/公斤，颗粒硅28元，尾部45元，多晶硅期货触及40元/公斤），电池片供需最好，光伏玻璃需出清2万吨。硅片报价已涨10%，电池涨2分钱，价格信号初现。
-**问**：人形机器人三季度有哪些催化剂信号？
-**答**：建议关注三类信号：华为云接入厂商、头部企业出货量、电机硬件优化。华为发布盘古世界模型和cloud robot平台，智元机器人拟借壳上市，宇树科技年收入突破10亿，智元、宇树中标中国移动1.2亿采购订单。
-**问**：游戏板块当前估值是否还有上行空间？
-**答**：当前A股游戏TTM PE约30倍（2023年AI行情45倍），2025年静态PE约20倍，估值仍有空间。6月版号发放158个为2018年以来单月最高，1-5月市场规模同比增长17%，调整后有望戴维斯双击，建议关注明年业绩确定性。</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>22868/3429</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="13.5" customHeight="1" s="9">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:10
+  </si>
+  <si>
+    <t>• 发言者 1 00:10
 请坐。
 • 发言者 2 00:11
 那今天这节课的老师要给同学们来讲一个主题班会，它的名字叫什么呀？梦想。那我们班有没有同学有哪些梦想呢？当保安。真的可以，同学们可以积极的发言，有什么梦想呀？要当喜剧男。要当喜剧人，在每一个班说的时候，每一个班的人都会有想当太空人。那说明这个广告词真的是深入人心。想当世界冠军。想当什么世界冠军。想当主角。那个一般他有的同学他说他想当一个歌手，所以我就刚刚让他上来唱了两首。对。班有没有同学想当歌手呀？
@@ -3646,66 +2667,9 @@
 那到时候我们再回过头来看一下我们的这个我们为什么现当下我们现在自己为什么会定下这些梦想呢？那好，那等一下每个小组的同学，第1个同学的老师把每个同学的梦想收一下，那这节课就上到这里了。同学们下课。
 • 发言者 4 36:26
 你们辛苦了。</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>课堂记录</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t># 梦想主题班会：教师分享追梦经历引导学生树立并坚持梦想
-## 课程概况
-本节班会课以“梦想”为主题，由教师主讲，面向班级全体学生。课程旨在通过分享个人追梦经历、组织互动讨论与观看视频案例，引导学生认识实现梦想所需的条件，鼓励学生树立并坚持自己的梦想。课堂以互动问答为主，学生积极参与，氛围活跃。 教师以“梦想”为引，询问学生们的梦想，学生积极回答，包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等。教师引出班会课内容包含5个大点，并以丑小鸭的梦想（变成白天鹅）作为引子。教师分享了自己的梦想——成为受学生喜爱的有名望的优秀人民教师，并讲述了自己过去的梦想清单：考中国美术学院、加入学生会、参加比赛、保持专业排名第一、考教师资格证等。教师介绍全民追梦时代，组织学生玩“梦想观察团”游戏，播放航模爱好者何宗发与普通歌手追梦的视频，引导学生讨论实现梦想的条件。最后，教师让学生写下自己的梦想清单并逐一展示点评，总结梦想需要量力而行、调整目标，通过努力和坚持实现。
-## 核心知识点
-### 1. 梦想的引入与定义
-- **班会主题与结构**：班会课以“梦想”为主题，内容包含5个大点；以丑小鸭的梦想（变成白天鹅）作为引子，引导学生思考梦想的意义。
-- **学生梦想示例**：当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等；教师指出每个班都有想当太空人的学生，并提及广告词深入人心。
-### 2. 教师个人追梦经历
-- **教师梦想**：成为受学生喜爱的有名望的优秀人民教师。
-- **过往梦想清单**：考中国美术学院、加入学生会、参加比赛、保持专业排名第一、考教师资格证等。
-- **考中国美术学院经历**：单考通过但未去就读，因离家远和家庭经济原因选择定向师范生，最终去了广东技术师范大学（原民族学院）。
- - 定向生免学费，不能考研但可在职考研，学费需自己交。
- - 高中时在国旗下讲话，当着全校面说一定要考上中国美术学院，当时很多人嘲笑，但最终通过努力实现了单考通过。
-- **大学自律坚持**：大学4年保持本专业排名第一（专业有41人），需要每天5点起床的坚持与自律。
-### 3. 实现梦想的条件
-- **全民追梦时代**：教师提到关于梦想的节目有《中国梦想秀》《超越梦想》《中国好声音》。
-- **“梦想观察团”游戏**：将4个大组分为4个观察团，观察对象是玩航模的小伙子和想成为歌手的普通人。
-- **航模爱好者何宗发案例**：中国唯一一个去法国巴黎比赛的航模爱好者，目标是带着飞机环游世界，把中国国旗挂在世界各大赛场上；计划在明年的世界锦标赛上再比高下；表演的飞机有真实原型机歼10。
-- **实现梦想的条件**：坚持、努力、勇气、机会、兴趣、能力、学习等。
-- **重要原则**：不要嘲笑任何人的梦想。
-### 4. 梦想的调整与坚持
-- **马云案例**：中考考了两次才考上高中，高考考了多次，但最终成为中国首富，说明起点高低不重要，关键在于坚持。
-- **马云的新梦想**：在未来的15年里，世界因他们而改变，享受改变他人的乐趣。
-- **梦想调整方法**：梦想可以一步步立高，如果目标实现不了可以调整，比如先考进年级前百再考前50。
-### 5. 梦想清单与总结
-- **梦想清单书写**：教师让学生拿出纸写下自己的梦想清单，并列出实现梦想所需的时间和收获。
-- **学生梦想示例**：考试不犯糊涂、考上重本/211、学医、成为设计师、大学4年攒20万、成为创业者、考630分、拥有健康身体、家人平安、世界和平、祖国越来越好等。
-- **课程总结**：梦想需要量力而行、调整目标，通过努力和坚持实现，追梦的人是充实的。
-## 问答记录
-- **实现梦想需要哪些条件**：坚持、努力、勇气、机会、兴趣、能力、学习等，缺一不可。
-- **起点低是否影响实现梦想**：不影响，关键在于坚持。马云中考考了两次才考上高中，高考考了多次，但最终成为中国首富。
-- **梦想实现不了怎么办**：可以调整目标，一步步立高，比如先考进年级前百再考前50。
-- **如何看待他人的梦想**：不要嘲笑任何人的梦想，每个梦想都值得尊重。
-## 课后任务
-- **课后作业**：写下自己的梦想清单，列出实现梦想所需的时间和收获；各小组第一个同学负责收齐本组同学的梦想清单，并交给教师。
-- **复习重点**：回顾实现梦想的条件（坚持、努力、勇气、机会、兴趣、能力、学习等），思考如何调整目标并坚持实现自己的梦想。</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>9362/1880</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="13.5" customHeight="1" s="9">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:00
+  </si>
+  <si>
+    <t>• 发言者 1 00:00
 【新思想引领新时代改革开放】以文化自信筑牢强国复兴精神之基建设中华民族现代文明
 • 发言者 1 00:14
 文化兴国运兴，文化强民族强。没有高度的文化自信，没有文化的繁荣兴盛，就没有中华民族伟大复兴。党的十八大以来，习近平总书记以强烈的文化自觉与历史担当，以重大理论创新指导具体实践，在“五位一体”总体布局中对文化建设作出战略部署，在全面深化改革中纵深推进文化体制改革，引领社会主义文化强国建设在正本清源、守正创新中取得历史性成就、发生历史性变革。全党全国各族人民文化自信明显增强，全社会凝聚力和向心力极大提升，汇聚起强国建设、民族复兴的磅礴精神力量。
@@ -3863,80 +2827,9 @@
 新时代新征程，上海、浙江坚定不移全面深化改革、扩大开放，在推进中国式现代化建设中走在前列。
 • 发言者 1 30:27
 今天（7月14日）的《全面深化改革中国式现代化万千气象》，让我们一起走进上海、浙江。</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议为新闻联播式综合播报，围绕全面深化改革背景下中国在各领域取得的成就与进展，以及国际动态展开。会议核心定调为展现中国在文化、经济、基础设施、外交等方面的积极发展，同时报道国际冲突与灾害事件。会议涵盖文化自信与文化建设、赵乐际访俄、夏粮产量、铁路货运、快递业、油气管网、防汛、国内联播快讯、国际新闻等多个主题，全面呈现中国式现代化建设的万千气象。关键决议包括：赵乐际访俄期间双方同意从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作；中央深入推进"藏粮于地、藏粮于技"战略，启动小麦单产提升三年行动；水利部针对"七下八上"防汛关键期逐流域安排防御，联合调度上游干支流水库群减小三峡水库入库洪峰流量。
-## 要点梳理
-### 1. 文化自信与文化建设
-- 党的十八大以来，习近平总书记对文化建设作出战略部署，推进文化体制改革，以文化自信筑牢强国复兴精神之基。
-- 2023年6月，文化传承发展座谈会系统论述中华文明五个突出特性，阐述"两个结合"意义。
-- 2023年10月，全国宣传思想文化工作会议首次提出习近平文化思想。
-- 《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案。
-- 《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。
-- 我国已成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力"新引擎"。
-### 2. 赵乐际访俄与中俄议会合作
-- 全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，出席中俄议会合作委员会第九次会议。
-- 赵乐际在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别会谈；今年是中俄建交75周年。
-- 双方同意从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作。
-- 中俄议会合作委员会第九次会议明确两国立法机构要密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作。
-- 普京表示俄中立法机构合作有助于推进双边合作优先议题；沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
-### 3. 夏粮产量与农业成就
-- 今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。
-- 夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤；小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高。
-- 中央深入推进"藏粮于地、藏粮于技"战略，全国已建成高标准农田10亿多亩，启动小麦单产提升三年行动。
-- 中央财政首次提前下拨16亿元小麦"一喷三防"资金。
-### 4. 铁路货运与快递业发展
-- 6月份，国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高。
-- 化肥农药运量同比增长26.2%；中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
-- 今年上半年，我国快递业务量超800亿件；快递企业已运行国际航线40余条，农村寄递网络覆盖范围逐渐扩大，每天超1亿多件快递包裹在农村地区流动。
-### 5. 油气管网建设与能源保障
-- 我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。
-- 西气东输四线今年投产后，年输气能力将提升150亿立方米；推进川气东送二线、虎林到长春天然气管道等工程。
-- 我国主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%；天然气"全国一张网"日供气能力超10亿立方米。
-- 到2025年，将初步形成东北、西北、西南以及海上四大油气战略通道，建成"五纵五横"天然气干线管网。
-### 6. 防汛工作
-- 重庆28个区县出现暴雨，其中13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江出现内涝、滑坡等险情，消防救援人员转移被困群众；安徽多条河流水位上涨，工作人员加强巡堤处置渗漏管涌。
-- 水利部针对"七下八上"防汛关键期逐流域安排防御，联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
-- 三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程。
-### 7. 国内联播快讯
-- 北京上半年320个市区重大项目全部开工，总投资超过4000亿元，聚焦现代化产业、基础设施、城市更新等领域，包括丽泽数字金融科技示范园、温榆河生态治理工程等。
-- 燕矶长江大桥北岸主塔封顶，主跨1860米。
-- 第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员参赛。
-- 内蒙古第34届草原那达慕开幕，以"相约草原遇见那达慕"为主题，持续到8月底。
-- "中非儿童手拉手"活动在京启动，来自五国儿童代表参加。
-### 8. 国际新闻
-- 美国前总统特朗普在竞选集会遭未遂刺杀，枪手为20岁左右男性。
-- 以军空袭加沙地带马瓦西地区致90人死亡，约300人受伤。
-- 加拿大东北部林火过火面积100平方公里，9600人被疏散。
-- 多国人士高度评价中国全面深化改革扩大开放取得的伟大成就。
-## 结论与决定
-- **中俄立法机构合作定调**：赵乐际访俄期间，双方同意从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作；中俄议会合作委员会第九次会议明确两国立法机构要密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作。
-- **粮食安全战略部署**：中央深入推进"藏粮于地、藏粮于技"战略，启动小麦单产提升三年行动，落实中央财政16亿元小麦"一喷三防"资金，保障夏粮稳产增产。
-- **防汛调度安排**：水利部针对"七下八上"防汛关键期逐流域安排防御，联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量，应对长江1号、2号洪水演进及三峡水库15日洪峰流量45000立方米每秒量级的洪水过程。</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>7755/2511</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="13.5" customHeight="1" s="9">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:03
+  </si>
+  <si>
+    <t>• 发言者 1 00:03
 现在来看讲义，首先呢我把我们在光学部分，因为咱们一共有三讲来学习光学，其实呢对于有些同学来说呢是新课，但还对于有些同学来说呢，今天这部分内容呢是一个复习。咱们在初中阶段的光学，不管是讲直线传播，还是光的反射，还是光的折射，实际上呢在我们物理上叫什么呢？叫几何光学。大家看这我们称之为这个也就是说这个几何光学呢应该说是人类从2000多年前就开始研究，比方像咱们今天要给大家，不管是讲新课还是复习的直线传播和反射，实际上在2000多年前的那个古希腊时期，那时候的哲学家们就已经找到这些规律了。
 • 发言者 1 01:00
 包括我们要讲的折射现象，还有咱们讲的折射规律，当然后人做的第1个工作是把折射规律变成折射定律。但是咱们初中阶段讲的还是规律，所以呢这是同学们要学的东西，今天可能会有点说老师怎么我们学的东西好几千年前就已经知道了，是这样，所以这是几何光学。然后等到同学们到了高中的时候，这部分知识以前高中也讲，但现在高中呢已经完全不讲了，他认为没有什么意义。其实也不对。我们其实照镜子呀大家戴眼镜其实还属于几何光学的范畴。
@@ -4158,84 +3051,9 @@
 后来的结果就电线就自个着了，所以呢还到处找呢，为什么自燃？实际上就是因为这个所以像咱们现在很多地方就是设计师他愿意用这种玻璃幕墙，为什么呢？因为设计师的设计费是根据你这个建筑成本来算的，你当然用玻璃幕墙比用砖头贵，然后呢咱们一般的人觉得好看就行，但是它缺点是什么呢？就有很多这种叫光污染。这种光污染有的时候就会引起很多种隐患，像很多树木什么就反而死了，而且呢你声音它都反射，所以有时候你会感觉到就在楼中间走，那噪音特别大，为什么所有的声音它发散不出，它通过这个凹面就反射回来了。
 • 发言者 1 01:43:30
 好，以及它的应用是透镜。今天咱们上到这，</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>课堂记录</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t># 初中物理光学复习课：核心概念梳理与习题巩固
-## 课程概况
-本节课为初中物理光学部分的复习课，由主讲教师系统梳理几何光学核心知识，涵盖光的直线传播、光的反射、平面镜成像及球面镜应用等模块。课程以知识框架导入，强调初中阶段光学属于几何光学范畴，并指出高中阶段将转向光的干涉、衍射等波动光学内容。教学过程中，教师结合大量生活实例、实验演示与习题讲解，帮助学生巩固概念理解，同时穿插视力保护、光污染等现实议题的讨论，课堂氛围轻松，师生互动频繁。课程核心学习目标为：掌握光沿直线传播的条件与光速差异，理解光的反射定律及作图方法，区分镜面反射与漫反射，掌握平面镜成像特点及实验方法，了解球面镜的应用与光污染问题。
-## 核心知识点
-### 1. 光学学习框架与光的直线传播
-- **光学学习框架**：几何光学从2000多年前古希腊时期开始研究；初中阶段学习几何光学，包括光的直线传播、反射和折射，高中阶段转向波动光学。
-- **光源分类**：光源分为自然光源（如太阳、萤火虫）和人造光源（如火把、蜡烛、电灯）。
-- **光线模型**：光线是物理模型，用带箭头的直线表示，并非真实存在。
-- **光沿直线传播**：光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。
- - 小孔成像成倒立、缩小的实像，与孔的形状无关，像的大小取决于物距与像距关系。
- - 日食时太阳、月球、地球在同一直线上，月球在中间；月食时地球在中间。
- - 大气层不均匀会导致光线偏折。
-- **光速**：光在真空中的传播速度为3×10^8米/秒，即每秒30万公里，一秒钟绕地球赤道7圈半。
- - 光在空气中的速度略小于真空，在水中约为真空中的3/4，在玻璃中约为2/3。
- - 太阳光最多能到达海洋约200米深度。
-### 2. 光的反射定律与作图
-- **反射定律**：反射光线、入射光线和法线在同一平面内；反射光线和入射光线分居法线两侧；反射角等于入射角。
-- **法线**：法线是垂直于镜面的辅助线，用虚线表示，并非真实存在。
-- **垂直入射**：光垂直射到镜面上时，入射角和反射角均为0度，此为常见易错点。
-- **作图方法**：先画法线，再根据反射角等于入射角确定反射光线或入射光线，作图痕迹（法线）需保留。
-- **例题结论**：第10题答案选C，第11题反射角为60度，第12题反射角为40度。
-### 3. 镜面反射与漫反射
-- **镜面反射**：平行光射到光滑表面，反射光平行，人眼只能在特定方向看到。
-- **漫反射**：平行光射到粗糙表面，反射光射向各个方向，人眼在任何方向都能看到。
-- **生活实例**：生活中的大多数反射是漫反射，如黑板、电影银幕、人的皮肤等；黑板反光是镜面反射，电影银幕是漫反射。
-- **判断水潭**：雨后夜晚，迎着月光走，发亮处是水潭；背着月光走，发暗处是水潭。
-- **光路可逆**：镜面反射和漫反射都遵守光的反射定律，光路具有可逆性。
-### 4. 平面镜成像及其应用
-- **成像特点**：正立、等大、虚像，像与物到镜面距离相等，连线与镜面垂直。
-- **实验方法**：使用玻璃板代替平面镜，便于确定像的位置；刻度尺用于比较像与物到镜面的距离；两段相同的蜡烛用于比较像与物的大小。
-- **虚像性质**：虚像不能用光屏接收，因为实际光线没有到达。
- - 第21题：视力表距镜3.5米，人距镜1.5米即可看到5米处的虚像。
- - 第22题：视力表距镜3米，人距镜2米。
- - 第23题：人距平面镜1米，人与像距离2米。
- - 第24题：人远离平面镜，像的大小不变。
- - 第18题：倒影属于光的反射，C选项（河水深度变浅）是折射。
-### 5. 球面镜及其应用
-- **凸面镜**：对光线起发散作用，成正立、缩小的虚像，应用于汽车后视镜、丁字路口转弯镜。
-- **凹面镜**：对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、太阳灶、耳鼻喉科检查镜。
-- **历史典故**：阿基米德利用凹面镜汇聚光线烧毁敌船。
-- **光污染**：玻璃幕墙形成凹面会汇聚光线，可能烧死树木、引燃电线，造成光污染。
-## 问答记录
-- **小孔成像的像与孔的形状是否有关**：无关，小孔成像成倒立、缩小的实像，像的形状取决于物体本身。
-- **日食与月食的形成原理**：日食时太阳、月球、地球在同一直线上，月球在中间；月食时地球在中间。
-- **垂直入射时入射角为多少度**：光垂直射到镜面上时，入射角和反射角均为0度，而非90度。
-- **虚像能否用光屏接收**：不能，因为实际光线没有到达虚像位置。
-- **人远离平面镜时像的大小是否变化**：不变，平面镜成像始终与物等大，与距离无关。
-- **雨后夜晚如何判断水潭位置**：迎着月光走，发亮处是水潭；背着月光走，发暗处是水潭。
-## 课后任务
-- **复习光的直线传播**：掌握光源分类、光线模型、光沿直线传播的条件与实例，重点复习小孔成像特点与光速在不同介质中的差异。
-- **复习光的反射定律**：牢记三线共面、分居两侧、反射角等于入射角，掌握作图方法，注意垂直入射时入射角为0度的易错点。
-- **复习平面镜成像特点**：正立、等大、虚像，像与物到镜面距离相等，连线与镜面垂直，理解玻璃板代替平面镜的实验原理。
-- **复习球面镜应用**：区分凸面镜（发散、缩小虚像）与凹面镜（会聚）的特点及应用场景。
-- **完成相关习题**：巩固第10-24题涉及的知识点，重点掌握各题答案与解题思路。</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>25691/2312</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="13.5" customHeight="1" s="9">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:14
+  </si>
+  <si>
+    <t>• 发言者 1 00:14
 电气工程基础是大家进入到专业课来的，所接触到的第1门课，也可以说是一门专业的入门课。我们这一门课程的教学目的，希望能够解决这样两个问题。第1个问题是希望大家能够掌握电力系统的4个典型的环节，包括发电输电配电用电这样4个典型环节的构成工作原理。以及与电力系统整体之间的关系，建立起电力系统的整体概念。这是第1个目标。第2个目标是希望大家能够掌握电力系统在分析设计运行管理这些方面的最基础的理论，最基本的技术以及基本的计算方法。
 • 发言者 1 01:05
 那么通过这样两个目标，等等最基本的工作。所以这一门课是我们专业的入门课，也是对大家今后工作非常重要的一门课程。这一门课的前修课程要求大家对电路理论和电机学的知识应该有一定的了解，特别是变压器和同步电机的相关知识，在我们这一门课上有比较高的要求。那么对这些方面有欠缺的同学，希望大家下去应该把相关的内容做一定的补充。我们这一门课学后还后面还有很多的后续课程，最重要的后续课程就是这样4门课。电力系统分析。
@@ -4329,90 +3147,9 @@
 比如说咱们华工变电站，面那个箱子里面装的，这也是个变电站，我们叫相似面。那么这样一个变电站它的电压等级是多少呢？10千伏变到380对吧？所以它是一个10千伏变电站。这样一个变电站。我们关山边上设了有一个变电站，它的最高电压等级是220千伏，所以我们叫做220千伏的变电站。就好像你们去参观过的是吧？在我们凤凰山变电站就在我们这边不远，凤凰山有一个变电站，你们好像也参观过，它的最高电压等级500千伏。
 • 发言者 1 43:54
 所以我们把它叫做500千伏的变电站，这是按照最高电压等级来进行分类的，这是一种方法。是按它的主要的功率，所流通的方向是从变压器的高压侧流向低压侧呢，还是从低压侧流向高压侧？那么我们把这个变压变电站，分为升压变压和降压变。变电站。如果这个辩论战的大家注意是最主要的功率，最主要的功率。那么大部分功率都是从高压侧向低压侧在传输，我们称之为降压变电站。反过来在发电厂里面，大部分功率是从发电机发出来的这个低压侧升压升到高压侧的，我们叫升压变电站。好，休息一下。</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>课堂记录</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t># 《电气工程基础》第一章导学与电力发展史讲解
-## 课程概况
-本次课程为《电气工程基础》第一章导学与电力发展史讲解。课程教学目的明确为两点：掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及其与电力系统整体的关系；掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术与基本计算方法。前修课程要求为电路理论、电机学，特别是变压器和同步电机知识；后续重要课程包括电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。第一章为全书概念最多、最重要的章节，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及其对设计运行的影响，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中心点接地方式。三个学习难点为：电能不能大量储存决定的有功无功动态平衡问题、额定电压规定的繁杂性、中心点接地方式对后续章节的影响。课程主体梳理了从直流输电到交流输电、再到现代交直流混合输电的电力发展演进脉络，并系统讲解了三相交流输电优势、电力系统形成过程、电网分类与变电站分类方法。
-## 核心知识点
-### 1. 课程教学目标与学习要求
-- **课程教学目的**：掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系；掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术与基本计算方法。
-- **前修课程要求**：电路理论、电机学，特别是变压器和同步电机的相关知识。
-- **后续课程衔接**：电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。
-- **第一章学习要求**：掌握电力系统、电力网、动力系统、变电站等基本概念；理解电力系统的特点及其对设计运行的影响；掌握电能质量指标及国家标准规定的范围；了解电力系统常用接地方式，特别是中心点接地方式。
-- **三个学习难点**：电能不能大量储存决定的有功无功动态平衡问题；额定电压规定的繁杂性；中心点接地方式对后续章节的影响。
-- **学习方法建议**：从基本概念内涵与外延入手，从电力系统特点与要求出发进行原理推导，寻找额定电压规定规律，比较不同中心点接地方式特点。
-### 2. 电力发展简史：直流输电阶段
-- **早期直流输电试验**：福泰勒使用2000米导线连接瓦斯发电机，拖动直流发电机、电动机和水泵，证明直流远距离输电可行。
-- **1874年**：俄国工程师在彼得堡建成4.5公里直流输电线路，传输功率4.5千瓦。
-- **1882年**：法国德普勒架设首条57公里直流试验线路，首端电压343伏、末端850伏，输送功率200瓦，损耗78%。
-- **1883年**：德普勒从法国南部进行14公里输电试验，输送功率1.1千瓦，损耗55%。
-- **1882年10月**：英国科学家发明直流输电三线制系统，外线与中线电压110伏，外线间电压220伏。
-- **直流输电技术限制**：电压等级低时损耗大、电压降落快，制造大容量高压直流发电机困难。
-- **19世纪末**：法国方剑串联多台直流发电机，将75千瓦电力输送75千米。
-- **20世纪初期**：瑞典科学家在串联直流发电机上安装短路器，实现不停电切换，此后20多年建成15条直流输电线路。
-- **1906年**：投运法国慕尼黑水电厂到里昂线路，180公里、57千伏、4700千瓦；1927年改建为260公里、125千伏、19000千瓦，接入两座水电站。
-### 3. 交流输电的兴起与交直流之争
-- **关键发明**：1876年俄国科学家发明单相变压器（主要用于照明）；1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行方式。
-- **直流电阵营**：爱迪生与凯尔文主张推行直流电，理由是直流电效率高、交流电有危险性（曾购买威斯汀豪斯交流发电机用于死刑实验）。
-- **交流电阵营**：威斯汀豪斯和特斯拉主张交流电，理由是交流电易用变压器升压降压、减少电能损失，交流发电机制造业发展为交流输电做了准备。
-- **1886年**：威斯汀豪斯在美国麻省进行1.2千米30千伏交流输电示范；在意大利建成17英里、2千伏高压输电线路。
-- **1886年**：俄国科学家发明三相交流电、三相交流输电和三相异步电动机。
-- **第一条交流输电线路**：法国到德国的交流输电线路，采用三相发电机和升压变压器，在法兰克福建两座降压变电站，一座供展览会照明，另一座供100马力三相异步电动机。
-### 4. 交流输电电压等级演进与直流输电复兴
-- **电压等级演进**：1898年发明真实绝缘子，美国加利福尼亚输电电压提高到33千伏；1906年发明悬式绝缘子，建成110千伏高压输电；1912年发现电晕临界电压与导线直径成比例，铝线和钢芯铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏输电线路；1936年美国287千伏线路投运；1952年瑞典建成380千伏线路，首次采用分裂导线；1956年苏联400千伏双回线路投入运行；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联特高压1150千伏线路投运，后降压至500千伏运行。
-- **中国交流输电发展**：224千伏线路1941年投运，330千伏1972年投运，500千伏1981年投运，1000千伏2009年投运（交流特高压首次）。
-- **直流输电复兴背景**：交流大电网稳定问题突出，直流输电在联网中的优势重新显现。
-- **直流输电复兴工程**：1954年瑞典本土与哥特兰岛建成世界第一个工业用海底电缆直流工程，电压100千伏、96公里，采用汞弧阀；1970年扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。
-- **中国直流输电工程**：第一个为舟山群岛与浙江定海电网连接；第二个为1989年葛上直流（葛洲坝电厂到上海），±500千伏；今年6月投运云广直流±800千伏特高压直流工程。
-### 5. 三相交流输电的优势与电力系统形成
-- **三相交流系统三大优点**：易于产生旋转磁场，三相电动机易驱动；瞬时功率恒定；输电线路导线（金属）消耗量最少。
-- **三相三线制优越性**：传输效率最高，金属消耗量在同等功率和功率因数下最小。
-- **电力系统形成过程**：从单机向附近负荷供电，到多机互联提高可靠性，再通过升压输电扩大供电范围。
-- **升压输电必要性**：输电线路参数（电阻、电抗）导致电压损耗和功率损耗，限制输电距离；升压可减小电流从而降低损耗。
-- **电力系统定义**：发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能。
-- **电力网定义**：电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络。
-- **动力系统定义**：电力系统加上发电厂动力部分（火电锅炉汽机、水电水轮机水坝等）。
-### 6. 电网分类与变电站分类
-- **地方电力网**：电压等级110千伏及以下（早期35千伏及以下），供电半径20~50公里。
-- **区域电力网**：电压等级110、220千伏及少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心。
-- **超高压远距离输送网络**：电压等级500千伏或1000千伏（东北有330千伏），任务是将发电厂电能远距离送到负荷中心，构成跨省跨地区大型电力系统。
-- **分类实例**：武汉电网属于地方电力网；华中电网属于区域电网；葛上直流、三峡到上海输电线路属于超高压远距离输电网络。
-- **变电站按最高电压等级分类**：华工变电站10千伏，关山变电站220千伏，凤凰山变电站500千伏。
-- **变电站按主要功率流向分类**：降压变电站（大部分功率从高压侧流向低压侧）、升压变电站（大部分功率从低压侧流向高压侧）。
-## 问答记录
-- **直流输电为何被交流输电取代**：直流输电电压等级低时损耗大、电压降落快，且制造大容量高压直流发电机困难；交流电易用变压器升压降压，可在电压提高状态下减少电能损失。
-- **为何最终采用三相交流输电**：三相交流系统易于产生旋转磁场使电动机易驱动、瞬时功率恒定、输电线路导线消耗量最少；三相三线制传输效率最高，金属消耗量在同等功率和功率因数下最小。
-- **为何需要升压输电**：输电线路的电阻和电抗导致电压损耗和功率损耗，限制输电距离；升压可减小电流从而降低损耗，扩大供电范围。
-- **电力系统、电力网、动力系统三者区别**：电力系统是发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能；电力网是电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络；动力系统是电力系统加上发电厂动力部分（火电锅炉汽机、水电水轮机水坝等）。
-## 课后任务
-- **课后阅读**：阅读主讲人推荐的三本电力发展史书籍，了解电力发展历程。
-- **复习基本概念**：掌握电力系统、电力网、动力系统、变电站等基本概念的定义与内涵。
-- **复习电力发展脉络**：梳理从直流输电到交流输电、再到交直流混合输电的演进过程，重点记忆各阶段关键工程节点与电压等级数据。
-- **攻克学习难点**：重点理解电能不能大量储存决定的有功无功动态平衡问题、额定电压规定的繁杂性、中心点接地方式对后续章节的影响。
-- **预习要求**：学完本章后仔细体会学习方法，从电力系统特点与要求出发进行原理推导，寻找额定电压规定规律，比较不同中心点接地方式特点。</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>11163/3977</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="13.5" customHeight="1" s="9">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:05
+  </si>
+  <si>
+    <t>• 发言者 1 00:05
 但这些东西本质上来说就是逗你玩的，对吧？就是故弄玄虚而已，所以他玩这一出的话呢，无非就是逗你玩。因为它的本质是下面那个东西。啊。而下面的东西又是通过另外一个东西观察到，但是他非不这么写，他就非要写成这种东西。这种东西其实是妨碍你理解的。但是会让你觉得magic.好朋友们大家好，欢迎来到频道，我是皮卡，那本期视频呢是一个新的系列的试水之作。新的系列的它的一个核心呢就是评论，那就是说我会带着大家去看一些网上的帖子，一些网友的关于一些数学问题的回答和尝试。
 • 发言者 1 00:48
 然后呢我会在里面给出我的评论，然后呢按照我的主观的想法去那那么接下来就带up主呢就带着大家来看一下这篇帖子，这个是发这个是提问在Stack exchange上面的，我经常提到这个网站，stack exchange.我简称为Mse mass stack exchange.这个呢是国外的一个非常有名的网站，它呢就是约等于这个知乎吧，但是我觉得跟知乎的定位是完全不一样的，因为这个网站上你只能提数学问题，而且只能提具体的数学问题。
@@ -4476,60 +3213,9 @@
 N+1分支1。那分子分母呢？分母也很简单，log1+n分支1嘛。对吧？这两个求极限太简单了。对吧？太简单了。那就是1。是不是？那就做了这个事情。但是我说实话，这个纯粹就是你先知道结果你才这么做的。当你不知道hn是一个怎样的变化率的时候，你让我猜你通过比如说计算一些数据，像高像欧拉那样，你算它个几十项，你大概知道是什么样子。如果你连猜都猜不出来的话，你你不可能去上来就蒙一个log n的。你我就说你凭什么不log log n的平方呢？
 • 发言者 1 27:17
 你凭什么不蒙个根号n呢对不对？去凑嘛。我觉得这个不自然，我觉得这个完全不自然，完全不自然。唉那么今天我们评论就讲到这里吧，这个后面还有很多方法，我们有机会再评论不过下，下次的话看反响吧，如果反响不错的话，我们出下一期我们可以再找一个帖子，再找一个话题来聊这个事。然后如果还不错的话呢，就是看看看网友的一些投稿吧。有网友去解决某些问题，他们的一些尝试思路之类的。</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>知识笔记</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t># 调和级数发散证明方法评述与数学评论系列试水
-## 知识概述
-本期内容属于数学分析领域，聚焦调和级数发散性的多种证明方法评述。核心探索命题是：面对同一数学结论，不同证明路径的优劣与自然性如何评判。整体推演框架以Stack Exchange上的经典问题为引，依次评述分组求和、对数下界、Stolz定理三类证明方法，穿插柯西凝聚判别法、积分估计等关联概念。主旨认知倾向为：数学证明应以揭示本质、促进理解为首要目标，技巧性过强、事后凑数的证明虽逻辑正确，但本质是故弄玄虚，妨碍理解。
-## 核心概念
-### 级数收敛与发散的定义
-- **收敛定义**：若级数部分和sn存在固定实数a，使对所有n均有sn&lt;a，则级数收敛。
-- **发散定义**：若存在单调递增且无界的下界bn，使sn&gt;bn且bn可任意大，则级数发散。该定义从高中数学角度切入，为不熟悉微积分的观众建立直观基础。
-### 分组求和证明
-- **核心思路**：将调和级数按项分组，使每组和大于1/2，因组数无限，部分和无上界，从而证明发散。
-- **与柯西凝聚判别法的关联**：柯西凝聚判别法的证明过程与分组求和完全一致，适用于非负不增序列，通过加速序列判断收敛发散性。
-- **思想延伸**：高斯求和1+2+...+100同样运用分组配对思想，体现"发现具有良好性质的组以简化求和"这一思路的普遍性。
-### 对数下界证明
-- **核心思路**：证明hn&gt;log(n+1)，因log函数无上界，故hn发散。hn为调和级数部分和的专用符号。
-- **积分估计流派**：利用积分曲线面积近似hn，hn的几何意义为矩形面积，始终大于曲边梯形面积。
-- **技巧性证明**：利用e^(1/k)&gt;1+1/k，通过连乘积化简为n+1。该证明被批评为本质是变魔术，通过障眼法让人感觉神奇，但妨碍理解。
-### Stolz定理方法
-- **定理定位**：中文称斯托尔兹定理，用于求分子分母无穷大时的极限。
-- **应用方式**：利用Stolz定理可证hn/log n的极限为1，从而证明hn与log n同阶、级数发散。
-- **方法评价**：该方法不自然，有先射箭后画靶之嫌——证明者事先知道答案，若不知道hn的变化率，不可能直接猜测log n。
-## 核心结论
-### 关键判断与结论
-- **证明方法优劣评判标准**：应以是否揭示数学本质、是否促进理解为首要标准，而非以技巧的炫目程度衡量。
-- **技巧性证明的定性**：利用e^(1/k)&gt;1+1/k连乘积化简的证明，本质是故弄玄虚、变魔术，通过障眼法制造神奇感，但妨碍理解，属于"逗你玩的"把戏。
-- **Stolz定理方法的局限**：该方法虽逻辑严谨，但因事先知道答案而缺乏自然性，属于先射箭后画靶。
-- **分组求和与积分估计的价值**：这两类方法思路自然、揭示本质，是值得推荐的证明路径。
-- **系列规划**：本期为数学评论系列试水之作，若反响不错将出下一期，继续评论其他数学问题。
-### 易混辨析与适用边界
-- **柯西凝聚判别法与分组求和的区别**：两者证明过程一致，但柯西凝聚判别法有明确适用前提——序列须为非负不增，分组求和则无此限制，适用范围更广。
-- **积分估计与差分的流派差异**：两者均为证明hn&gt;log(n+1)的可行路径，但积分估计通过几何直观揭示hn的矩形面积意义，差分则偏重代数操作，前者更利于理解。
-- **Stolz定理与前述方法的本质区别**：分组求和与积分估计从问题本身出发自然推演，Stolz定理方法则需预先知道结论方向，属于验证型而非发现型证明。</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>7465/1508</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="13.5" customHeight="1" s="9">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:05
+  </si>
+  <si>
+    <t>• 发言者 1 00:05
 Github不只是全球最大的同性交友平台，它其实是每个人都可以用的巨大的宝藏资源库，几乎我们想找的资源教程工具什么的，在github上都能够找到正经一点的，比如说麻省理工斯坦福等名校的公开课字节，阿里腾讯等大厂的面试题和面试经验。Google,阿里这些大公司最新的开源大模型，用AI搞副业赚钱的教程，AI学习资料等等，不正经的，比如说国内这些年缺网火爆的表情包大合集火到150岁养生指南，国内996最严重的大厂黑名单，还有不能播的。
 • 发言者 1 00:49
 那这次就让我们工作室的老李来带我们在
@@ -4575,70 +3261,9 @@
 GPT这类工具，比如我让ChatGPT帮我找github daily它会及时的分享各种最新最热门的项目。
 • 发言者 1 09:47
 好，这就是本期视频的全部内容了，上面提到的所有的开源项目，包括后面的教程，还有一些视频里面没有提到，但我们觉得很不错的项目都整理在文档里面了，需要的可以领取，这里是宣教我们下期见拜。</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>知识笔记</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t># GitHub实用资源分享与国内访问解决方案讲解
-## 知识概述
-本次分享围绕GitHub这一全球开源资源宝库展开，由工作室成员老李主讲，核心命题是帮助观众高效利用GitHub获取学习、工作与生活类资源，并系统解决国内用户访问GitHub时面临的网络不通、全英文界面、搜索功能不完善等常见问题。整体推演框架分为三个层次：先介绍多个实用热门开源项目，建立对GitHub资源价值的直观认知；再针对访问难题给出加速软件、镜像站、VPN三种解决方案及界面汉化手段；最后讲解项目页面结构与高效搜索方法，形成从资源发现到落地使用的完整路径。主旨认知倾向为：GitHub不仅是代码托管平台，更是覆盖教育、工具、娱乐、AI前沿等多领域的资源宝库，借助AI工具与合理方案可大幅降低国内用户的使用门槛。
-## 核心概念
-### GitHub资源生态
-- **资源覆盖范围**：GitHub上可找到麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂面试题与面试经验，Google、阿里等公司最新开源大模型，AI副业赚钱教程及AI学习资料，构成覆盖学习、求职、技术前沿的综合性资源池。
-- **项目本质**：GitHub项目本质为一个文件夹，项目名字下方为子文件夹或文件；每个文件标注最近commit日期即最近更新时间，若更新日期久远则大概率是无人维护的僵尸项目。
-### 实用开源项目
-- **工作性价比评估工具**：输入年薪、工作地区、年假、通勤时长、学历、工作年限及领导同事是否SB等因素，综合输出工作性价比分数与评级；老李以自身程序员经历测试获得"优质牛马"评价。
-- **表情包博物馆**：收集国内过去全网爆火的表情包大合集，涵盖甄嬛传、罗翔老师、特朗普、马保国等主题，便于斗图使用。
-- **健康指南项目**：分享经科学研究的健康知识，如间歇性进食促进胆汁代谢与炎症自愈、吃天然发酵类食品改善肠道菌群生态等。
-- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准的证件照和打印模板。
-- **健身指导项目**：提供自重、哑铃、弹力带、长凳等健身器材的替代方案，用户可选择练习肌肉群并获得参考动画；老李现场演示了自重练腹肌的动画指导。
-- **教材资源项目**：收集国内所有小学、初中、高中和部分大学的PDF教材，全部免费。
-- **全自动视频生成项目**：Morphing Printer Turbo，支持全自动视频生成。
-- **声音克隆模型ChatBox TTS**：零样本语言克隆，情感控制到位，克隆声音像真人说话。
-- **AI学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术，作者整理500多页PDF文档，含大量示意图。
-- **awesome AI Apps项目**：收录大模型最新Agent应用，如医学影像数据分析Agent、AI投资Agent、竞争对手情报分析Agent等。
-### 国内访问GitHub解决方案
-- **Watt Toolkit加速软件**：进入官网选择适合电脑系统的版本下载安装，打开后在网络加速中勾选GitHub加速即可流畅访问，为推荐首选方案。
-- **镜像站**：如gh-proxy，浏览器直接点开即可访问GitHub，默认显示镜像的项目地址，搜索其他项目不受影响；速度与稳定性稍逊，作为备选方案。
-- **VPN（魔法）**：老李个人最为推荐，但未展开具体操作说明。
-- **账号注册**：注册GitHub可使用国内QQ邮箱。
-- **界面汉化**：谷歌浏览器可安装谷歌翻译或沉浸式翻译插件，将网页翻译为中文；动手能力强的用户可安装汉化插件（同为GitHub上的项目）。
-### GitHub搜索与项目页面
-- **原生搜索局限**：默认按关键词精准匹配排序，例如搜索screen record与screen recording结果不同，导致搜索不全面；更常用的是按star数排序，star数代表项目受欢迎程度。
-- **AI辅助搜索**：推荐使用ChatGPT等AI工具，用中文提问（如"在GitHub上帮我找好用的录屏软件"），AI会总结成表格，提供更全面准确的结果。
-- **项目页面结构**：watch为关注项目，fork为复制项目到个人账号，star为收藏点赞；about为项目简介，release为软件安装包下载入口，read me文件为项目说明书，默认在项目最下方展开显示。
-- **热门项目发现**：通过explore中的trending可查看全站当天、本周、本月最热门项目；也可借助ChatGPT查找GitHub Daily，及时获取最新最热门项目推荐。
-## 核心结论
-### 关键判断与结论
-- **GitHub是综合性资源宝库**：覆盖名校公开课、大厂面试题、开源大模型、AI教程、教材与生活工具等多维度资源，价值远超代码托管本身。
-- **国内访问问题有成熟解决方案**：Watt Toolkit加速软件为首选方案，镜像站为备选，VPN为个人最推荐方案；注册可用国内QQ邮箱，界面可通过翻译插件或汉化插件解决。
-- **AI搜索优于原生搜索**：GitHub原生搜索按精准匹配排序存在遗漏，使用ChatGPT等AI工具以中文提问可获得更全面、更准确的热门项目汇总。
-- **项目活跃度可量化判断**：通过文件最近commit日期判断项目维护状态，更新日期久远大概率是无人维护的僵尸项目，应谨慎选用。
-- **会议决议**：分享GitHub实用项目并整理成文档供观众领取；推荐Watt Toolkit作为主要访问方案、镜像站作为备选；推荐使用AI工具进行GitHub搜索以解决原生搜索不全面的问题。
-### 易混辨析与适用边界
-- **watch、fork、star三者功能区分**：watch为关注项目动态，fork为复制项目到个人账号，star为收藏点赞；三者操作对象不同，不可混用。
-- **镜像站与加速软件适用场景**：镜像站适合快速浏览与搜索，但速度与稳定性稍逊；加速软件需下载安装，适合长期稳定访问；VPN为个人最推荐但未展开操作细节。
-- **原生搜索与AI搜索的边界**：原生搜索适合已知确切关键词的精准查找，AI搜索适合开放式需求探索；两者互补，AI搜索在结果全面性上明显占优。</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4014/2619</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="13.5" customHeight="1" s="9">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:07
+  </si>
+  <si>
+    <t>• 发言者 1 00:07
 锵锵三人行，首先得感谢马先生，马先生太好了，拉来一个他的朋友，但是这个朋友我更有兴趣跟你聊一聊，因为你是明朝那些事的作者，对，听着名字都像日本人当年明月是4个字，日本忍者，我觉得你是唉很少在电视上露面吧，
 • 发言者 2 00:27
 还经常不过就不是访谈类节目吧。
@@ -4992,75 +3617,9 @@
 非常有城府，你所以说我说这个人呢就看真的是被写坏的，就是嘉靖呢那个时候嘉因为明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的。这些人一般来说他都有某些程度的偏颇，因为如果你把它说太好，嘉靖上台先搞了个叫什么大礼仪事件，为这事死了很多人，可以说是也折腾了很多人，为什么就为给自己父亲争个名分，因为他父亲是王爷，他要把他追封为皇帝。所以说就是说历史就非常玄幻，就是我说的就是玄幻，就什么程度就是说有些事儿你看到你以为这么回事，实际上不是这么回事，对，所以
 • 发言者 1 38:31
 我就觉得看很多人专家写历史，我都觉得现在不爱聊说什么西方傲慢与偏见嘛，实际我看很多人研究历史就有傲慢与偏见，就是没有我同意你的观点就是说你没有设身处地，你老觉得你自个聪明，我判断他昏庸无能，对吧？其实这不是傲慢与偏见，我们能知道</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>采访记录</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t># 《锵锵三人行》纵论日本文化精神与明朝历史兴衰
-## 访谈概述
-本期《锵锵三人行》以日本历史剧《大奥》为切入点，围绕日本文化中的极端精神、忠诚文化与民族性格展开讨论，并与中国的中庸文化进行对比。随后话题转向明朝历史，嘉宾当年明月（《明朝那些事》作者）分享其研究明史的动机与见解，探讨明朝的兴衰、皇帝个性、社会风貌及历史研究的复杂性。整场对话以文化比较与历史解读为主线，穿插大量具体事例与个人观点。关于《大奥》，嘉宾认为该剧是继《大长今》之后最有影响的国外电视剧，制作严谨，群众演员不会笑。马先生指出日本战后用30年时间成为世界第二经济强国，源于全民族的极端精神；当年明月对比中日文化，认为中国讲究中庸，日本则坚持原则做到极致。关于日本民族对死亡的态度，当年明月认为日本民族不是藐视生命而是重视死亡，马先生补充日本经济危机时身家万贯的人剖腹自杀。话题转向明朝历史，当年明月解释自己研究明史是因为明史资料最多，并讨论明朝的兴衰、正德与天启皇帝的个性及历史研究的复杂性。
-## 访谈详细记录
-### 1. 开场与《大奥》讨论
-- **节目开场**：主持人感谢马先生带来朋友当年明月，并提及《明朝那些事》发行量在文学类排行榜第一。
-- **《大奥》的历史定位**：嘉宾认为该剧是继《大长今》之后最有影响的国外电视剧。该剧三部曲中，前两部对应中国晚明到清初，第三部在明治维新之前。
-- **日本历史剧的制作严谨**：群众演员不会笑，每个演员都极具专业精神。
-- **大奥的含义**：大奥即后宫，日语中“奥”指屋子最深处，即一般人不准进入的地方。
-- **幕府时期的权力结构**：日本幕府时期，天皇是摆设，实际权力掌握在幕府将军手中。德川家康开创德川幕府后，权力集中于一人。天皇曾因无钱举办活动向将军要钱被拒，甚至以退位抗议。
-### 2. 日本文化与民族精神探讨
-- **日本战后崛起**：马先生指出，日本战后用30年时间成为世界第二经济强国（绝对量），是必然结果，源于全民族的极端精神；日本是唯一没有资源的强国。
-- **中日文化对比**：当年明月认为中国讲究中庸，日本则坚持原则做到极致。
-- **日本经济现象**：日本人的跳槽率最低，很多公司实行终身雇佣制，但工作效率依然高。
-- **日本豆腐厂的例子**：规定当天做当天卖，夜里12点准时开始工作，所有人到点即起，一丝不苟。
-### 3. 日本忠诚文化具体体现
-- **阿福的例子**：25岁进大奥当奶妈，65岁去世，40年完全出于公心，不出于私心。
-- **“慢慢来才是最快的方法”**：当年明月认为这种文化思维方式是所有人按角色做事形成合力，最节省成本，不会互相抵消。
-- **日本商人的商业策略**：做绳子不赚钱铺市场，最终通过加价2%获得巨大利润。
-### 4. 日本民族性格与生死观
-- **对死亡的态度**：当年明月认为日本民族不是藐视生命而是重视死亡，马先生补充日本经济危机时身家万贯的人剖腹自杀。
-- **寻死的潜在欲望**：当年明月指出日本民族有寻死的潜在欲望，看樱花只看落的那天，对死亡不惧怕甚至向往，二战暴行是藐视生命的行为。
-- **文化差异的结论**：主持人提问是否愿意做日本人，嘉宾表示文化差异导致无法成为日本人。
-### 5. 明朝历史讨论
-- **研究明史的动机**：当年明月解释自己研究明史是因为明史资料最多。明史资料堆得比山还高，但一个事件可能有7个不同说法，如同罗生门。
-- **明朝的跌宕起伏**：明朝本身过程跌宕起伏，几次都要死没死了，如土木堡之变、夺门之变等，构成现代版电视剧。
-- **朱元璋的推崇**：朱元璋从乞丐到皇帝，是历史上独一份。当年明月推崇其因太不容易，且明朝规章制度基本由他定下。
-- **英雄史观的分歧**：马先生认为人的因素最大，改变时势一定是出现一个人；主持人质疑朱元璋的选择有逼上梁山的性质，当年明月强调历史最重要的是弄明白它是发生过的，不能套用经验教训。
-- **明朝兴亡**：嘉宾认为明朝经验体现在仁宣盛世及晚明市民生活富足。明末江南地区工商业兴起，市民生活轻松舒服，想去哪去哪，连皇册都不用了。金瓶梅、三言二拍等娱乐产品出现，说明有养活自己的资本。李自成起义是因为陕西一带发生大规模灾荒。明末工艺变得精细，日本派大量工匠与中国交流。
-- **历史经验教训**：当年明月认为“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，因为历史事件发生时有背景，史书只是照片，而古人的生活是录像，不能套用。
-### 6. 明朝皇帝与历史评价
-- **正德皇帝的评价**：当年明月认为正德皇帝并非史料所写的那么蠢，而是被嘉靖时期编史者（杨廷和等）偏颇记录。正德皇帝从江南回来在通州停留半天，先派人打探京城情况，说明其有城府。
-- **天启皇帝的木匠爱好**：天启皇帝爱好木匠，干完活让大臣去卖，还打听卖得怎么样，反映当时社会对家具的重视。
-- **朝代年限对比**：明朝276年，未跨过300年大限；宋朝（南北宋接上）延续319年，是唯一跨过300年大限的朝代。
-## 金句总结
-&gt; “我觉得日本民族它不是藐视生命，它是重视死亡，它是翻着的。”
-&gt; —— **当年明月** (回应关于日本民族生死观的讨论)
-&gt; “慢慢来才是最快的方法。”
-&gt; —— **当年明月** (解读日本忠诚文化中所有人按角色做事形成合力的思维方式)
-&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
-&gt; —— **当年明月** (阐述历史经验教训的局限性)
-&gt; “人的因素最大就是改变时势，一定是出现一个人。”
-&gt; —— **马先生** (表达英雄史观，以朱元璋为例)
-&gt; “他藐视生命，他很多人表示你为什么说二战时候日军到中国会有那么多暴行，它是一种藐视生命的行为。”
-&gt; —— **当年明月** (论证日本民族藐视生命的观点)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>14719/2452</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="13.5" customHeight="1" s="9">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>• 发言者 1 00:05
+  </si>
+  <si>
+    <t>• 发言者 1 00:05
 你好，我姓严，
 • 发言者 2 00:06
 是这里消化专科的医生，我想了解一下你的病情，先核实一下你的名字好吗？我叫张学恒，好，这样我就好称呼你。张先生你好，多大年龄了？48岁。那你这次来看病主要是哪里不舒服？
@@ -5380,60 +3939,9 @@
 要做胃镜的话，我想能不能给我安排在后天，因为我爱人她后天可以请假，我想有一个人陪同也比较方便一些，
 • 发言者 2 24:46
 那也行，我们后天也是做胃镜。的时间，那我们就可以先预约在后天吧，到时候你做了胃镜活检以后，正好我们张大夫查房，这样的话安排应该来说还是比较好的。那很好好的。那就这样子，我把你的情况先总结了，以后向张医生汇报，然后我们下一步再来讨论关于治疗的问题，你看你还有什么问题需要再询问我吗？其他的没什么问题了，没有什么问题了，那你就先休息好吧？好的，谢谢再见。</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>就医咨询</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t># 上腹反复疼痛伴黑便患者门诊问诊纪要
-## 就诊概况
-患者张学恒，48岁，因上腹反复疼痛4年、近3个月加重，伴两次黑便及近期呕吐，于消化专科门诊就诊。严医生系统采集现病史、既往史、个人史及家族史，初步考虑消化系统疾病可能，需进一步检查明确诊断。患者因婶婶患胃癌而担心自身病情，并顾虑手术对工作及出国进修的影响，医生予以解释安抚，并安排大便检查及胃镜检查。
-## 病史信息
-- **现病史**：上腹疼痛反复发作4年，每年春季多发，近3个月持续疼痛，位于心窝部，呈烧灼感，进食冷硬、辛辣食物或工作紧张时诱发，温暖轻松时无痛，无夜间痛醒。一年前及三个月前各出现一次黑便，每次持续约一个月，每日最多两次，大便形状基本正常，两次均住院治疗，住院后两三天大便转黄。近两个月呕吐数次，吐出酸味黄水样物，为当日早午餐食物，晚上腹胀欲吐，吐后舒适。
-- **用药史**：近期服用奥美拉唑（武汉药厂国产）、阿莫西林及所内医务室胃炎合剂，效果逐渐变差，奥美拉唑用量从每日两次每次一颗增至每日四五次。
-- **既往病史**：16岁时患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；无手术史。
-- **过敏史**：小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手出现红疹，持续半个月，确诊磺胺药过敏。
-- **系统回顾**：双眼近视400度，平时不常戴眼镜；偶尔口腔溃疡，贴小纸片可缓解；无头痛、咳嗽、心慌、关节痛等异常；偶因不洁饮食出现急性腹泻，很快好转。
-- **生活史**：出生于成都，一直在成都生活，在成都轻工研究所从事科研工作，工作紧张，经常加班熬夜。吸烟史：以前每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝；每天泡两次茶。26岁结婚，爱人及孩子身体健康。
-- **家族史**：父亲76岁，有低血压（90/60 mmHg）；母亲75岁，诊断冠心病，药物控制良好；弟弟身体健康。婶婶（叔叔的爱人）患胃癌，患者担心自己是否也会得胃癌。
-## 诊断结果
-- 初步考虑消化系统疾病可能，需进一步检查明确诊断。
-- 患者上腹疼痛反复发作4年，近3个月持续加重，伴两次黑便及近期呕吐，提示存在消化道出血风险，需评估出血情况。
-- 医生建议留大便进行便血检查，以评估消化道出血情况。
-- 胃镜预约在后天进行，胃镜活检后由张大夫（上级医生）查房，便于后续讨论。
-- 医生解释婶婶无血缘关系，不必担心遗传风险；表示需向上级张医生汇报后，再与患者商量下一步处理意见。
-## 治疗方案
-- **检查安排**：留大便进行便血检查，评估消化道出血情况；后天进行胃镜检查，因患者爱人后天可请假陪同；胃镜活检后由张大夫查房，进一步讨论治疗方案。
-- **生活方式指导**：患者吸烟量已从每天一包限制在10支以内，计划逐步戒烟；工作紧张、经常加班熬夜，需注意休息。
-- **用药指导**：近期服用奥美拉唑、阿莫西林及胃炎合剂效果逐渐变差，奥美拉唑用量已从每日两次每次一颗增至每日四五次，需待检查明确后调整用药方案。
-| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
-| --- | --- | --- | --- | --- |
-| 奥美拉唑（武汉药厂国产） | 每次一颗 | 每日四五次（原为每日两次） | 口服 | 效果逐渐变差，待检查明确后调整方案 |
-| 阿莫西林 | 未提及 | 未提及 | 口服 | 效果逐渐变差 |
-| 胃炎合剂（所内医务室） | 未提及 | 未提及 | 口服 | 效果逐渐变差 |
-## 预警信号
-- **复诊随访**：胃镜预约在后天进行，患者爱人请假陪同；胃镜活检后由张大夫查房，进一步讨论治疗方案。
-- **预警表现**：患者近3个月上腹持续疼痛，一年前及三个月前各出现一次黑便，每次持续约一个月，提示消化道出血风险，需密切观察大便颜色及性状变化。
-- **就医条件**：若再次出现黑便、疼痛加重或呕吐频繁等异常表现，需及时就医。</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>8519/1648</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="13.5" customHeight="1" s="9">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:05
+  </si>
+  <si>
+    <t>发言人 1  00:00:05
 现在开始法庭纪律，在合议庭审判长宣布开庭时，请诉讼各方参与人全体旁听人员起立，一是对法庭的尊重。二，诉讼各方参与人与全体旁听人。在执行任务中依靠服从法庭的指挥，尊重司法，遵守法庭纪律，不得实施下列行为，一鼓掌、欢呼，二吸烟、进食，三拨打。接听电话，四对庭审活动进行录音录像、拍照或使用移动通信工具等传播庭审活动，五其他危害法庭安全或妨害。
 发言人 1  00:00:45
 自己的什么？诉讼参与人发言的时候，应当经法庭许可。四、旁听人员不得进入审判活动区，不得随意站立、走动，需要发言的，应当。建议在庭审过程中，诉讼参与人的诉讼人的办法和秩序，情节较轻的，审判长可以警告、训诫、责令退出法庭。看春晚，集结每一个开心观众的心。请对谁上来可以打我的敌人。
@@ -6371,67 +4879,9 @@
 现代化。今天的庭审到此结束。闭庭后，请各方当事人。越看题目。没有，你用，我才能做，可以申请。所以。
 发言人 3  01:48:32
 现在闭庭。原题及亲子代表是代表。</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>庭审记录</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t># 国开行与东源电力等金融借款合同纠纷二审调解结案
-## 庭审概况
-本案系国家开发银行（以下简称国开行）因与云南东源电力股份有限公司（以下简称东源公司）、云南东源曲靖电力有限公司（以下简称曲靖电力）、招银金融租赁有限公司（以下简称招银租赁）金融借款合同纠纷一案，不服云南省高级人民法院云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，依据《中华人民共和国民事诉讼法》第一百三十四条第一款、第一百六十九条规定公开开庭审理。庭审围绕三个争议焦点展开法庭调查与辩论：国开行对案涉设备是否构成善意取得抵押权、罚息复利计算方式、东源煤电是否应连带给付违约金。各方就融资租赁登记性质、查询义务范围、设备唯一性等核心问题展开激烈辩论。合议庭在查明事实基础上提出调解方案，各方均无异议，当庭达成调解协议，本案以调解方式审结。
-## 诉辩意见
-**国开行（上诉人）**：主张其对案涉设备构成善意取得抵押权，罚息应计收复利，东源煤电应连带给付违约金。
-- 抵押设备为通用设备，无唯一标识码，无法逐一核查；已按央行规定查询融资租赁登记系统，未发现登记。
-- 动产抵押登记为法定登记，具有排他性；融资租赁登记仅为行业性规范，不产生物权效力。
-- 东源煤电利息支付截止2017年12月20日，国开行于2018年6月13日发送函件要求归还贷款本金，罚息应自2018年6月13日起算。
-- 借款合同第六条第四款明确约定罚息部分按照罚息利率计收复利，不违反法律强制性规定，应尊重意思自治。
-- 依据借款合同第24条第三项约定，东源煤电未按合同第13条、第14条配合办理账户管理及柜台签约手续，构成违约，应支付千分之一违约金，且违约金金额未超过法定最高标准。
-**东源公司（被上诉人）**：主张已履行告知义务，国开行应承担注意义务；罚息不应作为复利计算基数；违约金请求不成立。
-- 2015年12月2日通过邮件告知国开行抵押物存在融资租赁情况，邮件中设备名称相同且以红色标注，国开行作为专业金融机构应尽注意义务进行核查。
-- 借款合同第24条第二款第二项约定限期偿还而非立即到期，案涉本金近8.37亿元，当天发函要求当天偿还未给合理期限。
-- 引用《人民币利率管理规定》第21条及最高人民法院2015年、2016年判例，主张罚息不应作为复利计算基数，且复利再计复利无合同依据。
-- 国开行始终未举证证明东源煤电存在违约行为，且未按合同约定先行发出限期纠正通知，违约金请求不符合合同约定。
-**招银租赁（被上诉人）**：主张国开行未履行查询义务，不构成善意取得。
-- 国开行未按2014年93号文查询人行征信中心融资租赁登记系统；东源煤电与曲靖电力为全资控股关系，国开行应扩大审查范围。
-- 招银租赁2012年已取得租赁设备所有权，国开行抵押权于2015年设立，时间在后。
-- 融资租赁登记强化动产权利外观，可能产生对抗效力，但不影响所有权设立转移的法定效果。
-- 案涉五套设备因无唯一识别码未在登记系统中登记，但提交的附件清单载明设备存放地点为恩洪电厂，足以引起金融机构重视。
-- 其非借款合同违约金条款参与方，尊重合议庭审查结果。
-## 举证质证
-- **邮件告知事实核查**：东源公司出示2015年12月2日发送邮件，载明抵押物为恩洪电厂设备资产，抵押手续办理情况为登记，设备名称相同且以红色标注；国开行否认收到有效告知，主张抵押合同签订时间为2015年12月20日，晚于邮件发送时间。
-- **融资租赁登记查询核查**：招银租赁主张国开行未按2014年93号文查询人行征信中心融资租赁登记系统；国开行主张已按央行规定查询，2018年再次核查时曲靖电力公司名下仍无融资租赁登记，且其核查义务仅限于抵押人曲靖电力公司。
-- **设备唯一性核查**：招银租赁确认案涉五套设备因无唯一识别码未在登记系统中登记，但提交回租设备清单载明设备存放地点为恩洪电厂；国开行主张抵押设备为通用设备，无唯一标识码，无法逐一核查。
-- **融资租赁登记性质征询**：合议庭征询各方意见，国开行认为动产抵押登记为法定登记具有排他性，融资租赁登记仅为行业性规范；招银租赁认为融资租赁登记强化动产权利外观，可能产生对抗效力；东源公司认为融资租赁登记仅为行业指导性规范，不当然产生物权后果。
-- **利息计算核查**：国开行主张利息2179万5727.08元（2017年12月21日至2018年6月12日），罚息4105万零579.57元（2018年6月13日至2019年2月19日），复利191.8206万元（2018年3月21日至2019年2月19日）；东源公司主张罚息不应作为复利计算基数，一审判决已支持罚息复利部分，东源煤电未提起上诉。
-## 庭审结果
-- **调解协议达成**：各方当事人自愿达成调解协议，合议庭予以确认，庭后出具调解书。
-- **国开行债权确认**：国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元。
-- **招银租赁所有权确认**：招银租赁对涉案六项设备享有所有权，对应债权1377.4137万元。
-- **国开行抵押权确认**：国开行对93项设备享有抵押权。
-- **设备整体盘活处置**：招银租赁和国开行对案涉全部发电设备整体盘活处置，变现款双方各50%，费用各担50%。
-- **未实现债权清偿安排**：变现款不足清偿时，招银租赁未实现债权按破产重整计划预留方案清偿。
-- **司法变现不能处理**：双方放弃设备权益，由东源曲靖电力自主生产经营。
-- **一审判决确认**：一审判决第二项、第四项无争议，按判项内容确认。
-- **司法建议**：审判长指出本案反映的动产登记制度缺陷，将依据最高人民法院关于加强司法建议工作的意见向有关部门提出司法建议，共同推进国家治理现代化。</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>30731/2409</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="13.5" customHeight="1" s="9">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:25
+  </si>
+  <si>
+    <t>发言人 1  00:00:25
 画面是完整流程大公开。
 发言人 2  00:00:31
 各位，早上好。考生你好，欢迎参加今天的面试。今天的面试一共20分钟，回答4个问题。请合理把握好时间，逐题回答。答题时不要紧张，语言尽可能简洁明了。在你面前有一张题纸和草稿纸，请不要在题纸上做任何记录。如果你准备好了，现在就开始答题，请计时员计时。
@@ -6521,53 +4971,9 @@
 好，今天的面试到此结束，感谢你的参与。
 发言人 3  00:17:34
 谢谢各位考官，各位考官辛苦了。</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>面试报告</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t># 公务员结构化面试模拟：四题考察综合能力
-## 候选人概况
-本次面试为公务员结构化面试模拟，面试官主持，计时员负责计时，考生在规定时间内完成4道题目的作答。面试总时长20分钟，考生需逐题回答，合理把握时间，题纸和草稿纸可供使用，但禁止在题纸上做任何记录。考生在作答过程中整体表现完整，4道题目均按时完成，面试官在结束前3分钟提醒时间，考生确认无补充后，面试结束。四道题目分别考察综合分析能力、计划组织能力、应急应变能力和公共服务意识，考生均能结合公务员工作实际展开论述，作答结构完整、思路清晰。
-## 面试问答
-### Q1. 绳子比喻对公务员工作的启示
-- **面试官**：绳子对骏马、风筝、陀螺各有不同作用，请谈谈这对公务员工作有什么启示？
-&gt; **候选人**：绳子对骏马是鞭策，引申为自我反省，引用曾子"吾日三省吾身"强调反思对个人成长的重要性，提出单位应形成紧张、活泼、团结、有趣的风气，同事之间比较能力与效率而非物质。对风筝的解读聚焦权利与责任的平衡，提出治国理政中需建立权利清单、责任清单，确保权力运行有原则、有方法。对陀螺的解读联系公职人员"连轴转"的工作常态，指出责任感和成就感是支撑持续投入的内在动力，并以撰写长材料的经历为例，说明辛苦背后的价值感。
-### Q2. AI企业调研任务的组织
-- **面试官**：作为市政府办公室工作人员小王，请阐述如何组织一次AI企业调研？
-&gt; **候选人**：前期准备包括补充AI领域知识、学习兄弟城市调研经验、查阅国务院及省厅关于人工智能发展的指导意见。调研方案涵盖客观市场状况、服务需求、管理措施三部分。具体实施中，通过与企业对接阅读发展报告、设计调查问卷并请专家修改完善来摸清市场；通过召开座谈会听取企业在人才引进、政策倾斜、用地审批等方面的具体需求；管理措施方面，关注新兴经济可能带来的问题，如共享充电宝的信任危机，通过问卷调查摸排需要规范的政策方向。
-### Q3. 应对记者投诉的现场模拟
-- **面试官**：请现场模拟服务标兵小王答复记者关于管道反复堵塞的投诉。
-&gt; **候选人**：首先承认管道反复堵塞的事实，解释管道建于上世纪90年代，老城区改造难度大，夏季用水高峰导致问题集中。随后说明已联系维修师傅立即处理，并已将硬件问题汇报上级，计划通过城市综合保障工程改善基础设施。同时承认自身工作存在失职，请求媒体给予改进机会，并希望媒体向公众解释政府面临的难处和管道实际存在的问题。
-### Q4. 道路改造与雨污分流工程的社会矛盾处理
-- **面试官**：道路改造和雨污分流工程引发社会矛盾，请从公共服务角度分析并提出对策。
-&gt; **候选人**：将矛盾分为主要矛盾和次要矛盾，主要矛盾是时间上过去城市发展滞后导致当前需求不满足，次要矛盾包括噪音污染、出行问题和舆论不满。对策包括督促施工方加快进度、设置防噪墙、洒水降尘、建议替代道路、通过交通广播推荐路线、鼓励公交出行并增加公交班次，最后通过公告形式公开透明沟通，争取市民理解。
-## 能力评估
-| 评估维度 | 推荐评级 | 评估依据(具体事例) |
-| --- | --- | --- |
-| 综合分析能力 | 良 | 能从绳子对骏马、风筝、陀螺的不同作用分别引申出自我反省、权利与责任平衡、工作动力三层启示，并引用曾子名言、联系公务员工作实际展开论述 |
-| 计划组织能力 | 良 | 调研AI企业思路完整，涵盖前期准备、方案制定、实施调研三阶段，调研内容细分为客观市场、服务需求、管理措施三部分，方法具体可行 |
-| 应急应变能力 | 中 | 现场模拟答复记者投诉时承认问题、说明原因、提出立即维修与长期改善方案，但整体应对偏程式化，主动沟通与化解舆论的力度稍显不足 |
-| 公共服务意识 | 良 | 分析道路改造矛盾时能区分主要矛盾与次要矛盾，对策涵盖工程进度、噪音治理、出行优化、信息公开等多维度，体现较强的公共服务意识 |</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>5808/1642</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="13.5" customHeight="1" s="9">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:11
+  </si>
+  <si>
+    <t>发言人 1  00:00:11
 您早点过来排队，排队检票这个地方就是午门，这过去可不是斩首的地方，明朝皇帝在这杖打那些犯了错的大臣，清朝皇帝在这颁发第二年的历书，也叫颁朔之礼。从这个角度看，午门有三个门洞，进门之后您能看到，哎，变成五个门洞了，这就是我们常说的明三暗五，故宫跟天坛不一样，在这呢，皇帝是老大，所以中间那个正门。
 发言人 1  00:00:40
 只能皇上走，也有例外啊。皇上大婚的时候，皇后可以从这个门进一次。殿试考中前三名的，也就是状元、榜眼、探花，这哥仨可以从这门出去一次。旁边那两门走的是皇亲国戚和文武百官。进来之后，咱们现在的位置就是。这是太和门广场，眼前有五座金水桥。想过皇帝引的走中间，黄金国器走挨着中间这两座桥，文武百官走最边上。
@@ -6619,75 +5025,9 @@
 第二条游览路线是进门之后沿着中轴线往后走，看完了坤宁宫，咱们去看景仁宫和延禧宫，紧接着去逛钟表馆和珍宝馆。出来之后直奔御花园，完事呢从神武门就出去了，大概半天的时间就能逛完。最后一条路线比较适合那些时间有限，不想走太多路的朋友们，还是进门沿着中轴线往后走，看完了坤宁宫之后去储秀宫，出来去御花园，然后呢从神武门出，这条最省力的路线，预计2个小时左右就能逛完。
 发言人 1  00:12:49
 对于那些喜欢盖章的朋友们，我也给大家标注了七个可以免费盖章的位置，有需要的章友们可以截图保存。行了啊朋友们，关于故宫的。保姆级游览攻略到这就讲完了。如果您觉得这期视频对您有所帮助，求关注、求点赞、求转发，您的支持就是我最大的。</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>参观游览</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t># 故宫游览保姆级攻略讲解纪要
-## 参观概况
-本次讲解以故宫中轴线及东西六宫为主线，系统介绍了午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、寿康宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、延禧宫、御花园、神武门等核心景点的历史背景、建筑特色、文化典故与游览建议。讲解从午门检票入口出发，沿中轴线依次深入前朝三大殿与后三宫，再扩展至西六宫、东六宫及珍宝馆区域，最后经御花园至神武门出口。全程覆盖建筑功能、历史事件、宫廷生活细节及实用游览提示，并总结了三条不同时长的游览路线及七个免费盖章位置，为游客提供了一份完整的故宫游览指南。
-## 核心看点
-### 1. 午门与太和门广场
-- **午门**：故宫检票入口，明朝皇帝在此杖打犯错大臣，清朝皇帝在此举行颁朔之礼；建筑呈"明三暗五"格局，中间正门仅供皇帝通行，皇后大婚时可进一次，殿试前三名可出一次，两侧门洞供皇亲国戚和文武百官通行。
-- **太和门广场**：五座金水桥按等级通行，皇帝走中间，皇亲国戚走两侧，文武百官走最边；太和门为明朝皇帝御门听政之所。
-- **铜狮子**：太和门门口铜狮为故宫六对铜狮中最大的一对，象征权力，建议单独拍照而非合影。
-### 2. 太和殿、中和殿与保和殿
-- **太和殿**：举行盛大典礼的场所（皇帝登基、皇后册封），文武百官在广场高呼"吾皇万岁万岁万万岁"，站位遵循"文东武西"，西侧红衣阁为皇帝银库，东侧体仁阁为缎库。
-- **中和殿**：盛大典礼时皇帝的休息室。
-- **保和殿**：自乾隆五十四年起作为殿试考场；东北角汉字馆提供4枚免费印章，可购买《紫禁城100》现场盖章，但不同店铺印章不同且不能跨店盖章。
-### 3. 乾清门与后宫区域
-- **乾清门**：后宫入口，东侧为九卿直房，西侧为军机处；门口狮子耳朵耷拉、眉毛遮眼，警示后宫人员"不该看的不看、不该听的不听"。
-- **乾清宫**：皇帝寝宫，内设27张龙床以防刺客；牌匾"正大光明"后藏有立储诏书，皇帝写两份，驾崩后对比验证；门口铜鹤铜龟旁有江山金殿，为紫禁城最小宫殿，提醒皇帝以民生为本。
-### 4. 交泰殿、坤宁宫与西六宫
-- **交泰殿**：内放25块传国玉玺。
-- **坤宁宫**：皇后寝宫，明朝所有皇后均居于此，东北角文创店有5枚免费印章。
-- **储秀宫**：慈禧居住20多年的地方，现为慈禧五十大寿原状陈列，其子在此出生，旁边文创店有3枚免费印章。
-- **太极殿**：永寿宫西侧，是东西六宫中唯一称"殿"的建筑。
-- **慈宁宫与寿康宫**：慈宁宫为康熙为奶奶孝庄皇太后修建的养老院，旁为寿康宫（甄嬛居住地）。
-- **冰窖书吧**：有3枚免费印章，主讲人购买了冰溪图。
-### 5. 断虹桥、武英殿与文华殿
-- **断虹桥**：石狮子形态各异，最有名的为武当狮。
-- **武英殿与文华殿**：武英殿在西侧，后改为陶瓷馆，目前关闭；文华殿在东侧，有展览。
-- **箭亭**：清朝皇帝及子孙练习骑马射箭之处，旁边商店有文创雪糕。
-### 6. 钟表馆、珍宝馆与九龙壁
-- **钟表馆**：展示各种造型的钟表。
-- **珍宝馆**：为宁寿全宫，是乾隆的养老院，乾隆退休后仍每天上朝办公；并非单独展厅，院子周围屋子均有展品，游客众多，尤其凤冠展区拥挤；皇极殿为1:1复刻乾清宫，宁寿宫对标坤宁宫；养性殿后为乐寿堂，是故宫唯一能进去参观的皇家寝室，有二龙仙楼设计；珍妃井在出口附近，井口石为后加，珍妃并非从那个小眼进去；出口右手边商店有3枚免费印章。
-- **九龙壁**：我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头，因烧制损坏，工匠用木头刷白漆以假乱真。
-### 7. 东筒子夹道、延禧宫与御花园
-- **东筒子夹道**：适合拍照，为网红打卡地。
-- **延禧宫与景仁宫**：延禧宫为网红打卡地；景仁宫为甄嬛被封熹妃时所住，珍妃也曾居住。
-- **御花园**：有钦安殿，供奉真武大帝，紫禁城靠山景山酷似真武大帝像。
-- **神武门**：故宫北门，出门左手边有角楼咖啡（2枚免费印章）和故宫文创（2枚免费印章）。
-## 互动体验
-- **盖章体验**：全程共标注七个免费盖章位置，包括保和殿汉字馆（4枚）、坤宁宫东北角文创店（5枚）、储秀宫边文创店（3枚）、冰窖书吧（3枚）、珍宝馆出口商店（3枚）、角楼咖啡（2枚）、故宫文创（2枚）；不同店铺印章不同且不能跨店盖章。
-- **《紫禁城100》购书盖章**：在保和殿汉字馆购买《紫禁城100》并现场盖章，可选择邮寄到家或自行携带。
-- **文创雪糕**：箭亭旁商店有文创雪糕售卖。
-- **冰溪图购买**：主讲人在冰窖书吧购买了冰溪图。
-## 心得收获
-- **游览路线规划**：三条路线可供选择——全天路线走完所有景点，主讲人实际步行3万步；半天路线为中轴线+景仁宫延禧宫+钟表馆珍宝馆+御花园；2小时省力路线为中轴线+储秀宫+御花园。
-- **参观要点提示**：珍宝馆需进入院子周围所有屋子参观，重点观看凤冠展区；九龙壁左边数第三条白龙下可见木头修补痕迹。
-- **拍照建议**：太和门广场铜狮子建议单独拍照而非合影；东筒子夹道为网红拍照打卡地。
-- **通行规则认知**：午门门洞及金水桥均按等级划分通行路线，游客需注意相应规则。</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>4497/2226</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="13.5" customHeight="1" s="9">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:15
+  </si>
+  <si>
+    <t>发言人 1  00:00:15
 随着刚需房的推广，留守儿童问题逐步缓解，而留守老人的困境
 发言人 2  00:00:22
 却还
@@ -6815,55 +5155,9 @@
 在社区举办的送春联活动中，老书法家写下的福字，由孩子们传承，又传递给千家万户的留守老人。这大红的福字，承载着社工们为社区和谐付出的辛劳与汗水，连接着孩子、家长和留守老人，接续着尊老爱幼的中华传统，也象征着每一位国人对和谐社会的。解决养老问题绝非易事。这不仅需要政府的关心和重视，也离不开子女、社区乃至更专业的养老服务机构的耐心陪伴与关怀。
 发言人 1  00:41:08
 视频的最后，祝每一位老人都能安享晚年，病有所医，老有所养，住有所居，弱有所扶。</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>调研访谈</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t># 农村与城市留守老人养老现状调研及对策研讨
-## 访谈概况
-本次专项讨论会围绕农村与城市留守老人养老问题展开调研与研讨。调研者通过实地走访农村老人、村政府、民政局及城市社区社工，系统呈现了留守老人独居比例高、就医困难、经济压力大、精神孤独等现状，并对比了农村与城市在养老政策、社区服务、志愿者制度等方面的实践与困境。调研数据显示，65.5%的老人子女长期不在身边而无奈独居，仅26.8%的老人与子女同住；黑龙江绥滨独居老人因寂寞报警、杭州67岁独居老人去世数天后才被发现等案例，进一步印证了问题的严峻性。会议指出，解决养老问题需政府、子女、社区及专业养老服务机构协同发力，并提出了加强子女联系、丰富文化生活、建立老年协会、完善志愿者制度等具体建议。
-## 核心反馈
-### 1. 留守老人生活现状与困境
-- **独居比例高、无人照料**：65.5%的老人子女长期不在身边而无奈独居，仅26.8%与子女同住；独居老人面临无人照料、就医困难、意外风险等问题。黑龙江绥滨独居老人因寂寞报警、杭州67岁独居老人去世数天后才被发现，印证问题严重性。
-- **农村留守老人生活艰辛**：子女外出打工导致老人独居，经济压力大、适应能力降低，且面临城市中的无形歧视；村里60多岁老人仍从事喂鱼、喂猪等劳动。
-### 2. 农村养老政策与设施运营
-- **老龄化程度持续加深**：2021年当地73万多人口中17.8%为老年人，预计未来老龄化加剧。
-- **五保户供养标准有限**：分散供养五保户每月发放475元生活费，另有护理补贴，加上食补电补共600来块钱；一级二级残疾人纳入最低生活保障，标准分160、270、380元三档。
-- **养老设施运营经费无以为继**：农村养老面临经济困难、子女不在身边、娱乐方式少三大问题。此前探索建设的农村养老公共设施因地方财政困难，运营经费后续无支持，难以持续发挥作用。发言人2指出："地方财政都很困难，这种运营经费后续就没有支持的。"
-### 3. 城市社区养老实践与社工困境
-- **社区志愿者制度初见成效**：社区建立志愿者制度，采用一对一帮扶、定期表彰和积分兑换（如雷锋超市兑换礼品）等方式，并计划发掘中年志愿者；今年开展小手拉大手活动，从儿童青少年入手拉动家长参与；本周四开展送春联活动，邀请书法老师写对联，由孩子上门送给留守老人；去年中秋节开展做月饼活动，还做过百家宴。
-- **社工行业供给不足、专业欠缺**：城市社工分为社区社工（小区出资）和街道社工（政府出资）两类，每个街道和乡镇派两名社工驻点，但难以持续。社工工资低、项目资金不稳定，很多社工从业不超过一年便转行；湖南省每个街道花费十来万，省里虽拨钱但社工专业欠缺。发言人8反映："基本上很多同学就没做多久，基本上都垮了，可能不超过一年。"
-- **老人需要持续关爱**：社工分享的帮助心理问题老人的案例表明，单纯上门服务难以解决深层心理问题，老人需要持续关爱。
-## 核心洞察
-- **独居是留守老人面临的核心系统性风险**：子女外出务工与老龄化叠加，导致独居成为普遍状态，无人照料、就医困难、意外风险随之而来，且农村老人因经济压力大、适应能力降低而处境更为艰难。
-- **农村养老设施"重建设、轻运营"是普遍症结**：地方财政困难使设施运营经费缺乏持续保障，一次性投入后难以维持，设施难以真正发挥作用。
-- **社工行业"需求大、供给弱"的结构性矛盾突出**：社会需求量大而供给不足，工资低、资金不稳定、专业欠缺导致人才流失，行业难以持续发展。
-- **社区活动是撬动代际互动与社区和谐的有效抓手**：通过小手拉大手、送春联等活动，从儿童青少年入手拉动家长参与，连接孩子、家长和留守老人，接续尊老爱幼的中华传统。
-## 改进建议
-- **建立老年协会并保障运营经费**：建议建立老年协会，专项执行养老设施建设，保障固定场地和持续运营经费，避免一次性投入后难以为继。
-- **倡导子女多联系、丰富文化生活**：建议请专业施工人陪伴老人、倡导在外务工子女多联系、丰富文化生活，缓解老人精神孤独。
-- **完善志愿者制度并拓展参与群体**：社区志愿者制度采用一对一帮扶、积分兑换等方式，并计划发掘中年志愿者；2023年活动目标由家长自行组织，社区转为协助者角色。
-- **每个社区成立养老服务中心**：提供理疗、按摩、老年大学、心理咨询等服务，满足老人多元化需求。</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>5309/1841</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="13.5" customHeight="1" s="9">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:30
+  </si>
+  <si>
+    <t>发言人 1  00:00:30
 睡觉。
 发言人 2  00:00:38
 不是。做了这个水费险啊，你卫生不具备啊，不是200元啊，当然喝够喝完了的话不够了啊，我们再讲啊，大家讲的话是每周每周是每两周，是每个月是2块钱一块，
@@ -7453,68 +5747,9 @@
 这点我觉得
 发言人 2  00:49:14
 我们他们也会非常关注啊，都会主动问老师吧。今年是预报预报一些非常好了啊，比如我一包板子的话。一般都会说出来这个今年应该是我们的，但是他们他们教育这一块。大家如果没写的话，可以写。大家可以坐下，你看呃，如果有什么没听懂，然后各位家长如果有什么要补充的，也可以。</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>家校沟通</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t># 372班家长会：强化家校协同，共促学生成长
-## 沟通概况
-本次沟通为372班家长会，由班主任林瑞老师主持，面向全班60名学生家长（男生25人、女生35人）召开。会议旨在加强家校沟通，介绍班级管理与教育措施，促进家校合作，共同助力学生成长。会议围绕班级基本情况、教师团队、学生问题与解决思路、教育目标与措施、家庭教育建议及班级事务等议题展开。班主任指出学生处于初中阶段，生理心理持续变化，是不稳定时期，班级整体班风纪律良好，但存在少数学生周末玩手机、自习课效率低等问题。会议明确了费用收取方式、手机管理、安全教育等要点，家长代表张宇波分享了家庭教育经验，并讨论成立了家长委员会。整体沟通基调务实坦诚，聚焦学生成长与协同育人。
-## 沟通内容
-- **班级基本情况**：372班共60人，男生25人、女生35人；学生处于初中阶段，生理心理持续变化，是不稳定时期。
-- **班级优点**：时间观念和执行力强，班风班貌纪律良好。
-- **班级不足**：少数学生周末玩手机、自习课效率低、思考能力差。
-- **教师团队**：各科教师多为老教师和优秀教师，师范院校毕业，部分教师有3年以上教学经验，有的超过6年；班主任林瑞教授地理学科。
-- **书写问题**：个别学生书写差，建议家长购买字帖督促练习。
-- **自习课效率**：自习课效率低，将加强班委培训和人员管理。
-- **手机管理**：要求上交手机，家长可不定时打电话检查。
-- **网瘾问题**：发现少数男生有网瘾，曾充值400元玩游戏。
-- **违禁物品**：发现学生带镜子、看小说等问题，要求全部收掉。
-- **早恋关注**：建议家长关注学生QQ、抖音等社交账号。
-- **费用说明**：水费每月2元/人，每两周收取一次；已购买5本书，预交11000元尚未结算；未购买书箱的同学将退还相应费用；费用由学生交给生活委员，不在微信群转账。
-## 话题探讨
-- **手机管理与网瘾防范**：班主任要求上交手机，家长可不定时打电话检查；发现少数男生有网瘾，曾充值400元玩游戏，建议家长关注学生社交账号，防范网瘾和早恋问题。
-- **学习习惯培养**：针对个别学生书写差的问题，建议家长购买字帖督促练习；针对自习课效率低，学校将加强班委培训和人员管理。
-- **家庭教育方式**：家长代表张宇波分享经验，强调先做人、平常心、尊重孩子、多倾听交流，关注身体健康和心理健康。
-- **安全教育**：提醒学生注意交通安全，未满16周岁不得骑电动车。
-- **家长教育误区**：班主任建议家长避免过分关注、放任不管、过高期望等误区，多鼓励少批评。
-## 共识与配合
-### 学校推进
-- **班规管理**：制定详细班规，违规扣分、写检讨、罚站，严格请假制度，稳定学习秩序。
-- **班委培训**：加强班委培训和人员管理，提升自习课效率。
-- **手机管理**：要求上交手机，家长可不定时打电话检查。
-- **定期沟通**：班主任定期与家长沟通，了解学生表现。
-- **月考安排**：下次月考在11月初，由班主任组织相关工作。
-### 家庭协同
-- **费用配合**：由学生将费用交给生活委员，不在微信群转账；未购买书箱的同学将退还相应费用。
-- **手机监督**：家长不定时打电话检查学生手机上交情况，配合学校手机管理。
-- **社交账号关注**：关注学生QQ、抖音等社交账号，防范早恋和网瘾。
-- **书写练习**：为书写差的学生购买字帖，督促日常练习。
-- **安全教育**：提醒学生注意交通安全，未满16周岁不得骑电动车。
-- **心理健康**：关注学生心理健康，多鼓励少批评，避免过分关注、放任不管、过高期望等误区。
-- **保险购买**：建议家长自愿为孩子购买保险，约310元，可自行购买。
-- **电子学生证**：移动套餐78元，方便联系，能办则办。
-- **家委会成立**：至少需要3人，自愿报名，参与班级事务探讨，协助班主任与家长沟通。</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>17334/1657</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="13.5" customHeight="1" s="9">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:16
+  </si>
+  <si>
+    <t>发言人 1  00:00:16
 哦，已经开始录像了，刚开始录像。我发现这个录像得提前一点。Yeah. 哦，我应该先开始录像，然后再说话。好，现在我问一下，大家能听到声音吗？嗯。你开始录制应该就能听到，我这边就不打字问了。下面我说明一下本次会议的性质和定位。本次会议是一个周会，10月28号周。
 发言人 1  00:00:53
 然后周会的主题是总结工作，你看一下会议的等级是一个自愿级。嗯目前就这定义为这样子就可以。然后会议资料是这三个，然后我念一下吧，会议资料是工作报告，这班看法，还有这班型社区介绍，然后会议目标是初步统一成员意见，你要通过这次会议统一。我们对这个社区的认识。然后那个更好看，然后美观一点，然后。
@@ -7578,63 +5813,9 @@
 然后换7028上的屏幕。这个就是最后的讨论。因为我自己学自己学也可以，我想和大家一起学。那多长时间一个小时了，那我们要不就继续在线下继续吧，我们一起学，这个时间也长了。我会。我们要下一个。看一下我们的会议目标啊。会议目标是。通过统一。对，一直听不到。邀请同事会邀请同事在村村的队。
 发言人 1  00:55:28
 音乐放的什么？如果一个人。地图。退货完成。开完了会，回到班级，我背后的同学叫我的名字，把我叫到走廊里，说。放歌，我还要最后放歌。都不想出去。</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>团队例会</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t># 周会总结工作并统一社区认识
-## 例会概况
-10月28日召开团队周会，会议等级为自愿级，主题为总结工作。会议资料包括工作报告、这班看法、这班型社区介绍。会议目标为初步统一成员意见，统一对社区的认识。会议围绕社区建设、教育团队组建、执法队伍组建、课程开发、活动策划等任务展开讨论，并就服务定价权、待遇、休假等具体问题形成初步共识。工作方向方面，计划将服务定价权交给消费者，改为代购模式，以提升服务质量与效率，并强调需要政府资源支持。具体任务方面，目前有四个任务，包括课程开发、组建执法队伍、大运发放等，下个月主要任务是组建执法队伍。社区介绍方面，计划修改社区介绍，将“我们是谁”提到最上面，并提及抖音任务和可视化学习方案。整体推进态势良好，部分议题仍需后续确认。
-## 工作进展
-### 工作方向与模式调整
-- **服务定价权调整**：计划将服务定价权交给消费者，改为代购模式，以提升服务质量与效率。
-- **政府资源对接**：强调工作开展需要政府资源支持。
-### 教育团队与赛事筹备
-- **教育团队组建**：计划组建教育团队，并协调相关资源。
-- **互联网+创业大赛**：计划参加互联网+创业大赛，作为近期重点推进事项。
-### 执法队伍组建
-- **执法队伍组建**：下个月主要任务为组建执法队伍，该任务最为重要，需确保顺利推进。
-- **任务分配**：负责安排任务分配，确保执法队伍组建工作有序开展。
-### 课程开发与活动策划
-- **课程开发**：目前有四个任务，包括课程开发，负责课程开发任务并协调教育团队组建工作。
-- **大运发放**：负责大运发放的调试工作，并统计活动费用。
-### 社区介绍与宣传
-- **社区介绍修改**：修改社区介绍，将“我们是谁”提到最上面，强调使命感、目标感、主要任务感、成员要求。
-- **宣传方案**：提及抖音任务和可视化学习方案，作为社区宣传的辅助手段。
-### 待遇与休假安排
-- **待遇标准**：上班5000元，额外有奖励和提成。
-- **休假安排**：休假为周五半天加周末两天。
-## 落实安排
-- **纲领章程修订**：负责修订纲领章程，确定路线，并安排任务分配，确保执法队伍组建工作顺利推进。
-- **社区介绍修改**：负责修改社区介绍，将“我们是谁”提到最上面，并完善使命感、目标感、主要任务感、成员要求等内容。
-- **同事邀请与方案制作**：负责邀请同事加入，共同制作解决方案，并安排后续线下学习事宜。
-- **大运发放调试**：负责大运发放的调试工作，并统计活动费用。
-- **课程开发与教育团队**：负责课程开发任务，并协调教育团队组建工作。
-## 未决风险
-- **工作方向调整**：工作方向可能偏颇，需要调整，需持续关注方向与实际情况的匹配度。
-- **任务分配差异**：任务分配存在条件差异，可能影响执行进度与公平性，需在后续安排中予以平衡。
-- **线下学习安排**：是否继续线下学习未确定，需进一步确认。
-- **同事加入安排**：邀请同事加入的具体安排未明确，需后续细化落实。</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>4999/1297</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="13.5" customHeight="1" s="9">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:08
+  </si>
+  <si>
+    <t>发言人 1  00:00:08
 你好，呃我姓严，是这里消化内科的医生，嗯我想了解一下你的病情，先核实一下你的名字好吗？
 发言人 2  00:00:16
 我叫张春和。
@@ -8074,58 +6255,9 @@
 没有什么问题了哈。那你就先休息，好吧？
 发言人 2  00:25:24
 好的。谢谢。</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>就医咨询</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t># 消化内科首诊问诊：上腹烧灼痛伴黑便呕吐，商定隐血与胃镜检查
-## 就诊概况
-患者张春和，男，48岁，于消化内科门诊就诊，由严医生接诊，为首次问诊。主诉上腹烧灼样疼痛反复发作4年，每年春季多发，近3个月加重，伴两次黑便及近期呕吐宿食。疼痛位于心窝处，进食冷、硬、刺激性食物或工作紧张劳累时诱发，与油腻食物关系不大；近3个月疼痛为白天发作，夜间无痛醒，疼痛可忍受。近3个月出现两次黑便，分别发生于一年前和三个月前，每次持续约一个月，均住院治疗，住院后大便转黄。近两个月出现呕吐，呕吐物为酸水样，含当日或前日食物，夜间呕吐后舒适。医生初步判断需排查上消化道出血及器质性病变，针对患者对胃癌遗传风险及手术必要性的担忧进行解释安抚，最终商定留取大便标本行隐血检查，并将胃镜检查预约至后天，以便患者爱人陪同，检查后由上级张医生查房讨论后续治疗方案。
-## 病史信息
-- **既往病史**：16岁时患甲肝，在三医院确诊，住院一个月，出院时肝功能正常，此后体检肝功均正常；小时候因扁桃体炎在儿童医院就诊，服用磺胺药后左手起红疹伴瘙痒，持续半个月，医生诊断为药物过敏，此后禁用磺胺药。
-- **预防接种**：按计划完成，近两年单位统一接种乙肝疫苗（上海产），共三针，无不良反应。
-- **用药史**：曾服用斯达舒，初始有效，后效果不佳，剂量从每日两次每次一颗增至每日四五次仍无效；近期加用奥美拉唑（国产，武汉药厂）和阿莫西林，以及单位医务室自配胃炎合剂，服药有效但停药后复发。
-- **系统回顾**：偶有头昏，与休息有关；双眼近视400度；偶发口腔溃疡；无咳嗽咳痰、无心慌心累；偶有急性腹泻；小便正常；关节肌肉无疼痛；记忆力正常。
-- **生活史**：出生于成都，一直在成都生活，未到过传染病疫区；工作单位为成都轻工研究所，从事科研工作，工作紧张，经常加班熬夜；吸烟史：以前每天一包，现限制在10支以内，计划逐步戒烟；饮酒：偶尔应酬饮酒，平时不喝；喝茶：每天泡两次淡茶。
-- **家族史**：父亲76岁，有低血压（患者自述血压90/60）；母亲75岁，有冠心病，服药控制良好；有一个弟弟，身体健康；一位婶婶（叔叔的爱人）患胃癌，患者因此担心自己是否也患胃癌。
-## 诊断结果
-- **初步印象**：上腹烧灼样疼痛反复发作4年，近3个月加重，伴两次黑便及呕吐宿食，需排查上消化道出血及器质性病变，建议行大便隐血检查及胃镜检查以明确诊断。
-- **家族遗传风险分析**：医生解释婶婶为叔叔的爱人，与患者无血缘关系，不必担心遗传风险。
-- **手术必要性判断**：患者担心是否需要手术，因工作繁忙且单位可能安排出国进修，希望尽早安排；医生表示需待检查资料全面后再判断是否手术，若药物能控制则无需手术。
-## 治疗方案
-- **检查安排**：患者需留取大便标本进行隐血检查，以排查出血；胃镜检查预约至后天进行，因患者爱人可请假陪同，检查后恰逢张医生查房。
-- **后续诊疗安排**：医生将总结病史后向上级张医生汇报，再商定下一步治疗意见。
-- **用药指导**：患者近期服用奥美拉唑（国产，武汉药厂）、阿莫西林及单位医务室自配胃炎合剂，服药有效但停药后复发，具体用药方案待检查结果明确后由医生进一步调整。
-| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
-| --- | --- | --- | --- | --- |
-| 奥美拉唑（国产，武汉药厂） | 未提及 | 未提及 | 未提及 | 服药有效但停药后复发 |
-| 阿莫西林 | 未提及 | 未提及 | 未提及 | 与奥美拉唑联合使用 |
-| 斯达舒 | 每日两次每次一颗，后增至每日四五次 | 每日四五次 | 口服 | 初始有效，后效果不佳，已停用 |
-| 胃炎合剂（单位医务室自配） | 未提及 | 未提及 | 未提及 | 服药有效但停药后复发 |
-## 预警信号
-- **复诊随访安排**：胃镜检查预约至后天进行，检查后由上级张医生查房讨论后续治疗方案；医生将总结病史后向上级张医生汇报，再商定下一步治疗意见。
-- **需密切观察的预警表现**：患者近3个月出现两次黑便，分别发生于一年前和三个月前，每次持续约一个月，需警惕上消化道出血复发；近两个月出现呕吐，呕吐物为酸水样，含当日或前日食物，夜间呕吐后舒适，需关注呕吐症状变化。
-- **需及时就医的处置条件**：若再次出现黑便、呕吐加重或出现其他新发症状，应及时就医；患者因工作繁忙且单位可能安排出国进修，希望尽早安排检查，医生表示需待检查资料全面后再判断是否手术。</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>10297/1897</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="13.5" customHeight="1" s="9">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:14
+  </si>
+  <si>
+    <t>发言人 1  00:00:14
 开宗明义的讲，就是大家关心的这些问题，其实啊并不是我们关心的问题，也不是我们正在研究的问题。啊这个里面呢，其实我要是讲的是包含两层意思。那第一层意思就是首先从我从投资者的角度去出发，就就他者的角度去出发。啊我要讲的就是其实大部分人关心的类似的这种就What happen next的这样的问题呢。
 发言人 1  00:00:37
 就是说你其实你听到的这个答案呢，对你来说其实没有太大的这个用处。为什么这样说呢？比如说比方讲我看好一个板块，我看好哪个个股，啊然后我告诉你我很看好，这个对我来说呢，我看好这个东西呢是基于相关的知识，对我来说这个东西叫knowledge，但是对于你来说，你得到的仅仅只是一条肖楠看好某某这个信息。
@@ -8447,80 +6579,9 @@
 大家。
 发言人 2  01:09:22
 谢谢。嗯，下面我们有请第二位分享嘉宾蔡荣成总，简单介绍一下蔡总。</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>专题讲座</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t># 基金经理肖楠路演：反对抱团与均值回归，聚焦四大方向研究布局
-## 讲座概况
-本次路演中，基金经理肖楠向机构投资者系统阐述其研究框架与投资理念。肖楠开宗明义指出，投资者关心的“What happen next”问题并非其研究重点，因为答案对投资者而言只是信息而非知识，二者之间存在巨大鸿沟。他提出自己的研究框架将问题分为重要不重要、可研究及难以研究四类，真正关心的是标的基本面是否变化、投资逻辑是否更新、认知是否更深入领先、投资框架是否值得修正。在投资理念层面，肖楠明确反对市场上流行的“抱团”与“均值回归”两个观点，认为收益率长期呈幂律分布，投资核心在于寻找长线超级牛股。他回顾过去一年在互联网、财富管理、新消费、高端制造四大方向的研究布局，并分享对投资框架的五点反思与更新，涵盖商业模式理解、终局判断、长期变量、深度价值及企业增长曲率（X factor）等维度。最后，肖楠就中期投资机会、伟大公司判断标准、全市场基金选股逻辑、血制品行业、农林牧渔行业、商增商减分析、增长曲线、财富管理行业及企业家精神等问题回答了投资者提问。
-## 核心观点
-### 知识与信息之间存在巨大鸿沟
-- **研究框架的出发点**：投资者关心的“What happen next”问题并非研究重点，因为得到的答案只是信息而非知识，对投资决策帮助有限。
-- **问题四分类法**：将问题分为重要不重要、可研究及难以研究四类，以此界定研究边界。
-- **真正关心的核心**：标的基本面是否变化、投资逻辑是否更新、认知是否更深入领先、投资框架是否值得修正。
-### 反对“抱团”与“均值回归”
-- **“抱团”定义不本质**：基金经理之间是竞争关系，主观上不可能抱团；同一公司买同一板块是研究员推荐被认可的结果，并非抱团。
-- **“均值回归”仅为局部正确**：均值回归在90%的时间正确，但10%的错误代价惨重；长期看收益率呈幂律分布，应寻找长线超级牛股。
-- **幂律分布的直接证据**：美国股市200年价值增量由4%的公司贡献，若剔除这4%的公司，美国股市200年没有上涨。
-- **波段操作的教训**：某商学院老师在海螺水泥上做波段，过去十年赚两三倍，但2016-2017年卖出后，股票两年涨了五六倍，再也没买回来。
-### 四大方向研究布局
-- **互联网**：全球只有中国和美国能做成巨大互联网产业，中国已迭代三代企业（流量、运营、算法），未来仍有大机会；港股通开通后可投资更多公司。
-- **财富管理**：中国进入小康，人均收入中位数提升5%-10%将带来巨额剩余财富，行业空间远超想象。
-- **新消费**：新一代消费公司从CEO到组织架构、经营理念与传统企业完全不同，未来会越来越多。
-- **高端制造**：中国是全球几乎唯一拥有全产业链的国家，在众多细分领域已占据主导地位，未来空间可见。
-### 投资框架的五点反思与更新
-- **对商业模式理解的不足**：世界上没有一劳永逸的坐地收钱生意，长期看所有企业都会死去，单一维度可能错失机会。
-- **对终局判断的反思**：从商增角度理解商业模式可能更本质，企业成长过程中靠什么吸收熵增是重要问题。
-- **对长期变量的认知升级**：存在一些特别长期的变量（如国运、文化背景）解释了相当一部分收益率来源，应保持谦卑并研究这些变量。
-- **对深度价值有效性的质疑**：深度价值只是结果，导致深度价值的原因不变，最好的结果也就是不输，可能长期无效。
-- **对企业增长曲率（X factor）的重视**：企业增长存在曲率，经典投资模型没有变量估计曲率，这些X factor无法定价但长期起作用。
-## 金句总结
-&gt; “均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。”
-&gt; —— **肖楠**（论证反对“均值回归”观点时，说明其局部正确但长期代价惨重）
-&gt; “基金经理之间是竞争的关系。其实是竞争的关系，你你让我跟你报。在一起本身这件事情就其实是不太可能。”
-&gt; —— **肖楠**（反驳“抱团”观点时，强调基金经理之间是竞争关系而非合作关系）
-&gt; “深度价值它只是一个结果，是导致这种深度价值的原因不变，那么深度价值，那么它最好的得到的结果也就是不输了。”
-&gt; —— **肖楠**（反思深度价值有效性时，指出其作为结果而非原因，长期可能无效）
-## Q&amp;A 环节
-**主持人**：关于中期投资机会，您怎么看？
-**肖楠**：承认曾错过一些机会，因终局判断悲观而放弃，但复盘发现即使终局不好，中期仍可做出漂亮投资，未来会争取把握。
-**主持人**：如何判断一家公司是否伟大？
-**肖楠**：伟大公司无法从财务指标中看出。举例A、B两家公司，A公司研发投入高、技术迭代快，有产业报国情怀，堪称伟大。
-**主持人**：全市场基金的选股逻辑与消费基金有何不同？
-**肖楠**：选股逻辑与消费基金完全一样，都是基于不可能三角、企业三阶段、三种商业模式等。
-**主持人**：如何看待血制品行业？
-**肖楠**：壁垒不是特别强，研究不深，建议请教其他基金经理。
-**主持人**：如何看待农林牧渔行业？
-**肖楠**：行业提升是因为牧原股份，不是看好整个行业。
-**主持人**：如何理解商增商减？
-**肖楠**：用企业部门增多、效率变差、腐败出现等例子解释商增概念，并建议读党史学习处理商增。
-**主持人**：如何看待增长曲线？
-**肖楠**：举例顺丰在疫情时能送快递、美的在疫情时占有率超过格力，说明曲率拐点的重要性。
-**主持人**：如何看待财富管理行业？
-**肖楠**：行业分层，财富分布极不均匀，头部公司可能拿走行业增量的绝大部分，可能诞生特别大的企业。
-**主持人**：如何看待企业家精神？
-**肖楠**：要谨慎归因，不要轻易给企业家精神定价，应在客观归因穷尽后再考虑，且只在两两比较时使用。</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>26252/2459</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="13.5" customHeight="1" s="9">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:14
+  </si>
+  <si>
+    <t>发言人 1  00:00:14
 正方四辩王新峰，正方 RUC棒辩论队向大家问好。下面有请反方做自我介绍。嗯嗯，这是介绍了半天，我们就不讲了，我们作为这个城市，在这个城市，那我爸爸就是直接从地方的公司换成了，就是也是整个。首先是不是爱他，你说爱是。王老师对我们的理想对象有更大的要求，刚刚说的，当他出现的时候，我就没有希望要求他。
 发言人 1  00:01:08
 他会说，你什么？他就会尽量，就是，但是在之前，他是不觉得，他会让我去爱上去，去不爱上去的。所以说，他。第二个我们来是安全的，安全的，同时告诉大家，这个是成绩确实是一个配方，一个配方是高的，是对于过去的这个时间的地点。都会怎么样？可能某一天春光正好，你穿着白衬衫出去穿越了阳光洒在沙滩上，你突然就爱上了他。
@@ -8668,54 +6729,9 @@
 多少人终其一生连这个迷药的味道都没有尝过，他只能清醒，会用自己的理智去判断，找一个。过日子，这才是最美好的一个精神。并且去去精心的熬制这款秘药给你的那个名字，并小心的使用它，守护这个后院通道的医生和战士。我要把这个，我要把这个桌子给放平。你爱的人会爱上谁，可是他会爱上谁，那个人对他好还是坏，爱他还是不爱他，你都不知道啊，你这么爱他的人，你怎么放心把他交给一个未知的某某某呢？
 发言人 1  00:53:11
 你受得了吗？好吧。你重新先试一下。</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>辩论会</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t># 辩论赛：拥有让人爱上自己的超能力应不应该使用
-## 辩论概况
-本场辩论赛围绕“如果拥有让任何人爱上自己的超能力，应不应该使用”这一辩题展开。正方RUC棒辩论队主张应该使用，反方则持反对立场。双方围绕爱的本质、自由意志、占有与真爱、超能力的作用机制等核心议题展开激烈交锋。正方将爱定义为超自然、非意志控制的力量，类比月老红线、丘比特金箭等神话意象，认为超能力客观存在，能帮助人们获得真爱，并强调使用超能力的前提是真心爱对方。反方则质疑超能力机制，认为其本质是洗脑和精神控制，剥夺了对方的自由意志，更像占有而非爱，并以强奸类比强调违背对方意志介入亲密关系的不道德性。在质询与自由辩论环节，双方围绕爱的标准、放手的爱、超能力使用后的风险等展开攻防。最终正方获胜，获得4分钟总结时间。
-## 各方立场
-### 正方（RUC棒辩论队）
-- **爱是超自然、非意志控制的力量**：正方将爱定义为超自然力量，类比月老红线、丘比特金箭等神话意象，认为爱是缘分，是身体力行，而非理性选择。正方四辩王新峰指出：“因为爱一个人就是自己意志的产物，到目前为止，对方都没有向我们论证，在您方的世界里，我只要意志在爱这个人，到底发生怎样的作用。”
-- **超能力机制是改变自己或创造条件，而非洗脑**：正方认为超能力客观存在，其作用机制更可能是改变自己或创造条件，而非反方所主张的精神控制。
-- **使用超能力的前提是真心爱对方**：正方强调使用超能力必须出于真爱，超能力能成就真爱、避免遗憾；同时承认若相处不合适会选择放手。
-### 反方
-- **超能力剥夺自由意志，本质是占有**：反方认为超能力是洗脑和精神控制，违背对方意志，更像占有而非爱。反方以强奸类比强调不道德性：“这个人原来不爱你的，但是你打了响指，他就一定爱上你了。这个和很多有必要的强奸犯讲的道理是一样的。”
-- **爱应基于自由选择**：反方主张爱应建立在对方自由意志的基础上，超能力导致对方失去选择权，因而不应使用。
-## 核心争议
-### 爱的本质：意志控制还是情非得已
-- **反方**：预设爱可由意志控制，质疑超能力剥夺对方自由意志，本质是洗脑和占有，违背对方意志介入亲密关系不道德。
-- **正方**：指出反方预设了错误前提，强调爱是情非得已、坠入爱河，而非理性选择；超能力机制是改变自己或创造条件，而非洗脑，且使用前提是真心爱对方。
-### 超能力的使用机制与道德边界
-- **反方**：以强奸类比，认为超能力如同“打了响指就让对方爱上自己”，与“有必要的强奸犯讲的道理是一样的”，本质是违背意志的强制介入。
-- **正方**：回应称爱本身不受意志控制，超能力只是改变自己或创造条件；使用超能力的前提是真心爱对方，并非强制占有。
-### 放手的爱与超能力的风险
-- **反方**：质疑超能力导致对方失去选择权，提出放手的爱才是真正的爱。
-- **正方**：强调爱是玄学，超能力能避免遗憾；承认若相处不合适会选择放手，回应反方对风险的质疑。
-## 结辩裁决
-- **正方结辩**：回顾反方论证漏洞，强调爱是超自然力量，超能力能成就真爱，且使用超能力是出于真爱，论证超能力使用的正当性。
-- **评委点评**：正方获胜，获得4分钟总结时间。</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>12403/1363</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="13.5" customHeight="1" s="9">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:10
+  </si>
+  <si>
+    <t>发言人 1  00:00:10
 所以做了这个手术之后做了八期的化疗，在复查的时候就发现有肝转移，从老家又来到北京做了个派的CT，
 发言人 2  00:00:19
 发现有
@@ -9055,55 +7071,9 @@
 觉得现在挺好的。对，他就觉得挺好。嗯。嗯。愿意提升。嗯。提升免疫力靠自己啊。是。面对是有限的，大夫也是有限的啊，咱手术也做了，现在就是。怎么帮助他用这个事，这个把责任啊放到自己，我跟他说了，他要给你做免疫评估，但是你方案你来定，看人家对不对。
 发言人 1  00:16:35
 他咋做免疫评估，是问一个问的，今天早上查了一个。早上查了个血。</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>就医咨询</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t># 结肠癌术后复发转移患者治疗方案讨论与基因检测决策
-## 就诊概况
-患者为结肠癌术后复发转移病例，于2023年9月因结肠癌行切除手术，术后完成8期化疗。术后复查发现肝转移，从老家转至北京行PET-CT检查，并于去年9月接受肝消融及乳腺结节切除。因存在腹膜转移（切肠时可能未切净），术后行紫杉类化疗，但仅完成首次检查，后续因肝功能异常停药3个月。3月底复查显示肝脏、肺及腹膜仍有转移，4月份检查提示转移较广泛；上个月肠镜未见异常，但PET-CT提示转移，医生认为肠镜可能未做准确。本次专项讨论会围绕后续治疗方向展开，医生初步判断当前主要问题为全身系统治疗，建议通过第二次基因检测获取精准治疗依据，并优先于局部介入。
-## 病史信息
-- **既往病史**：2023年9月因结肠癌行切除手术，术后完成8期化疗；术后复查发现肝转移，行PET-CT检查；去年9月行肝消融和乳腺结节切除；存在腹膜转移，切肠时可能未切净。
-- **用药史**：消融和乳腺结节切除后行紫杉类化疗，因肝功能异常，仅完成首次检查，后续停药3个月。
-- **近期复查**：3月底复查显示肝脏、肺及腹膜仍有转移；4月份检查提示转移较广泛；上个月肠镜显示无异常，但PET-CT显示有转移，医生认为肠镜可能做得不好。
-- **生活史**：患者尚不知晓病情扩散，不愿接受过多检查；家属表示患者今早已抽血检查。
-## 诊断结果
-- **初步判断**：当前主要问题是全身系统治疗，介入不是主要问题；转移较广泛，涉及肝脏、肺及腹膜。
-- **基因检测评估**：患者既往曾做过基因检测，但可能不够全面；医生强调基因检测可提高检出率，对选择靶向药和免疫治疗有指导意义，建议进行第二次基因检测。
-- **免疫评估建议**：医生建议进行免疫评估以了解免疫细胞状态，具体方案由家属决定。
-- **检查评估**：上个月肠镜未见异常但PET-CT提示转移，医生认为肠镜可能未做准确；针对家属询问是否需要再做核磁等检查，医生认为当前应关注患者状态，避免过度检查。
-## 治疗方案
-- **基因检测安排**：决定进行第二次基因检测，可联系肿瘤医院直接进行；建议将既往切片与本次切片共同送检，以对比治疗前后基因变化，获取更精准的治疗依据。
-- **全身系统治疗**：确定当前治疗方向为全身系统治疗（化疗、靶向、免疫），优先于局部介入；免疫联合靶向治疗可能产生协同作用（1+1），并提及结肠癌三线药物联合免疫治疗的机制。
-- **免疫评估**：建议进行免疫评估，结合今晨抽血结果，由家属决定是否进行及具体方案。
-- **生活方式调整**：关注患者身体状态调整，提升免疫力；可使用四联康等药物改善肠道问题。
-| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
-| --- | --- | --- | --- | --- |
-| 四联康 | 未提及 | 未提及 | 未提及 | 用于改善肠道问题 |
-## 预警信号
-- **复诊随访**：建议进行第二次基因检测，获取检测结果后用于指导后续治疗；家属需与患者沟通免疫评估事宜，结合今晨抽血结果决定具体方案。
-- **病情观察**：3月底复查显示肝脏、肺及腹膜仍有转移，4月份检查提示转移较广泛，需密切监测转移进展。
-- **就医条件**：患者因肝功能异常曾停药3个月，后续治疗中需关注肝功能状况；患者尚不知晓病情扩散，家属需关注其心理状态与身体状态调整。</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>7063/1429</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="13.5" customHeight="1" s="9">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:45
+  </si>
+  <si>
+    <t>发言人 1  00:00:45
 大哥。欢迎来到海尔洗机创新
 发言人 2  00:01:06
 发布会，
@@ -9249,49 +7219,9 @@
 浴巾暖烘烘，贴身衣物温软亲肤。洗衣不打扰，夜晚也能安静洗。一体集成，我家的阳台洗衣房。
 发言人 3  00:37:39
 我不喜欢湿漉漉的夏天。妈妈说她有一个好办法。哇，这就是。我们的新阳台吗？这些新朋友们好像都会魔法，让阳台变得整洁明亮，再也不用挂满衣服。我的小熊朋友也变得干干净净，家里飞舞的毛毛消失不见了，空气都那么清爽。以后这里就是我们的秘密基地了。yeah.</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>产品发布</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t># 海尔发布洗干集成新物种迭代H2 双旗舰定价公布
-## 产品概况
-海尔洗衣机创新发布会正式推出洗干集成新物种——迭代H2洗干集成机。该产品基于全球用户洗护需求洞察，针对中国80%用户将洗烘套装在阳台叠放使用所引发的屏幕过高、开门方向相反、水盒太高太沉等操作不便，以一体集成机身重塑阳台洗护场景。发布会以产品演示与用户场景展示为主，强调其为海尔为中国家庭打造的原创之作，核心价值在于提升家庭整洁有序与美好生活体验。产品专为客阳一体家居风格设计，集成洗涤、烘干、护理等多种功能于一体，搭载智慧大脑、灵犀洗烘联动、3D透视烘干、精华洗2.0等创新技术，覆盖从洗涤、烘干到健康护理的全流程需求，目标人群为追求家务解放与家庭健康品质生活的中国消费者。
-## 市场定位
-- **目标受众画像**：面向中国家庭用户，尤其是采用客阳一体家居风格、将洗烘设备置于阳台的家庭；同时覆盖渴望解放家务的年轻人、对洗衣液残留敏感的母婴人群、养宠家庭及有宝宝的家庭。
-- **核心用户痛点**：中国80%用户将洗烘套装在阳台叠放使用，存在屏幕过高不便操作、开门方向相反、水盒太高太沉等使用痛点；洗烘套装叠放存在震动等安全隐患；传统烘干存在烘干不彻底、需二次晾晒的问题。
-- **典型使用场景**：阳台嵌入标准橱柜的客阳一体空间；大件衣物（羽绒服、水洗被）一次烘透场景；养宠家庭去除衣物线屑毛絮场景；对噪音敏感的家庭洗涤甩干烘干全过程场景。
-- **差异化优势**：区别于传统洗烘套装的分体叠放形态，迭代H2以一体集成机身从源头解决叠放安全隐患与操作不便；167厘米高度适配中国用户平均身高，无需踮脚操作；超薄机身嵌入60厘米标准橱柜全平不突出，兼顾美观与整洁；同向开门设计尊重既有使用习惯；无水盒设计免除手动倒水负担。
-- **核心价值主张**：集成不仅是外观一体化，更是使用体验的进化——以智慧大脑实现上下桶默契配合，以灵犀洗烘联动缩短烘干时长，以3D透视烘干实现大件一次烘透，为中国家庭打造整洁有序的美好生活。
-## 核心卖点
-| 维度 | 核心卖点 | 关键参数 |
-| --- | --- | --- |
-| 一体集成设计 | 专为客阳一体空间设计，一体集成机身解决洗烘套装叠放带来的震动等安全隐患，同向开门取放流畅，无水盒设计免手动倒水 | 机身高度167厘米；超薄机身嵌入60厘米标准橱柜，全平不突出 |
-| 智慧互联 | 搭载全新升级智慧大脑，中枢神经式智能网络实现上下桶默契配合；灵犀洗烘联动数据共享，缩短烘干时长 | 洗涤结束前上桶提前15分钟主动预热 |
-| 烘干技术 | 原创双擎热泵技术大件烘干不缠绕；首次引入行业领先3D透视烘干，羽绒服、水洗被可一次烘透，免去二次晾晒 | 10kg烘干容量；3D透视烘干技术 |
-| 洗涤与健康 | 升级精华洗2.0提升洗衣效率；新鲜净水漂洗减少洗衣液残留；空净过滤系统去除线屑毛絮；三台变频电机降低全过程噪音 | 39分钟洗净一周衣物；三台变频电机覆盖洗涤、甩干、烘干全过程 |
-## 发售信息
-- **版本与定价**：迭代H2推出两款配置——10kg 3D透视烘干款定价12998元；10kg 双擎热泵款定价10998元。
-- **产品定位**：海尔为中国家庭打造的原创之作，核心价值在于提升家庭整洁有序与美好生活体验。</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>7311/1387</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="13.5" customHeight="1" s="9">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:13
+  </si>
+  <si>
+    <t>发言人 1  00:00:13
 好吧。同志们，先把手机调成静音，我们今天开会。同志们，今天召开中共巢湖市银屏镇白母山村芦塘支部党员大会，改选中共巢湖市银屏镇白母山村芦塘支部委员会，支部共有党员8名，其中正式党员8名，有选举权的。应是因病请假一名，迟到会有选举权的党员7名，符合法定人数，可以开会。
 发言人 1  00:00:58
 应邀参加今天会议的有。银坪镇党委组织委员钱小丽同志，让我们以热烈的掌声表示欢迎。现在我宣布，中共巢湖市银屏镇白母山村芦塘支部委员会换届选举党员大会现在开始，请全体起立，奏
@@ -9477,71 +7407,9 @@
 服务基层服务群众。最后我代表新一届党支部希希望大家对我们如何开展工作提出建议和意见，更希望大家能够对我们工作中的不足提出批评。再一次感谢各位领导及公司的对我们的信任和支持。好同志们，巢湖市银屏镇白母山村卢塘党支部党员大会经过全体党员的共同努力，已完成了大会的任务。
 发言人 1  00:29:56
 现在我宣布中共巢湖市银屏镇白母山村。堂支部委员会换届选举大会圆满结束，请全体起立奏国际歌。</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-中共巢湖市银屏镇白母山村芦塘支部委员会换届选举党员大会于2019年10月12日召开。支部共有党员8名，其中正式党员8名，有选举权的党员7名（因病请假1名），符合法定人数。镇党委组织委员钱小丽到会指导，代表镇党委提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。会议听取并审议通过上届支部委员会工作报告，依次通过选举办法、候选人名单及监票人计票人名单，经竞职演说、无记名投票，选举产生新一届支部委员会委员和书记，并对委员进行分工。新当选支委代表发言后，大会在奏国际歌中圆满结束。
-## 要点梳理
-### 1. 会议开场与领导讲话
-- 主持人宣布会议议程，确认党员人数符合法定要求，邀请镇党委组织委员钱小丽讲话。
-- 钱小丽代表镇党委提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。
-### 2. 上届支部委员会工作报告
-- 上届支部委员会作三年工作报告，总结成绩与不足，经党员讨论后鼓掌通过。
-- 思想政治建设：大力加强思想政治建设和理论学习，扎实开展"两学一做"学习教育常态化、制度化和"讲严例"专题警示教育活动。
-- 组织制度建设：严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度；三年来新发展党员1名，按规定收缴党费2640元上交上级党组织。
-- 党风党纪建设：积极开展党务公开，推进党内民主建设；认真抓好党风党纪教育，筑牢拒腐防变思想防线。
-- 存在不足：党建工作制度不够完善、党员主体意识尚需提高、党支部对党员教育管理监督不够深入。
-### 3. 通过选举办法与候选人名单
-- 会议通过党员大会选举办法，规定选举中共芦塘支部委员会委员3名，候选人4名，差额1名，差额比例不少于20%。
-- 选举采用无记名投票方式，先差额选举委员，再等额选举书记；参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；候选人得到赞成票数超过实到会有选举权人数的半数方可当选。
-- 经镇党委批复，支委候选人预备人选为卢燕娇、辛东升、杜军强、秦磊，书记候选人预备人选为卢艳娇。
-- 会议通过监票人贾淑玲，计票人员黄婷丽、刘彩云。
-### 4. 候选人竞职演说
-- **卢艳娇**（1993年9月出生，2014年4月入党）：承诺加强支部建设、推动村集体经济发展、抓好民生工程。
-- **杜军强**：强调农村党支部是桥梁纽带，承诺担当主带角色为党员群众服务。
-- **辛东升**：承诺群众有困难随叫随到，严格要求自己，圆满完成上级任务。
-- **秦磊**：强调责任心强、思想觉悟高，承诺配合上级工作，不计较个人得失。
-### 5. 选举新一届支部委员会
-- 大会进行支部委员选举，实到会有选举权党员7名，发出选票7张，收回选票7张，选举有效。
-- 计票结果：卢艳娇6票、杜军强6票、秦磊2票。
-- 选举结果：卢艳娇、辛东升、杜军强当选为新一届支部委员会委员。
-### 6. 选举书记与委员分工
-- 召开第一次支部委员会全体会议，通过书记选举办法，卢艳娇以3票当选为新一届党支部书记。
-- 分工明确：辛东升负责组织宣传工作，杜军强负责纪检工作。
-### 7. 新当选支委代表发言与大会闭幕
-- 新当选支委代表发言，感谢党员信任，表示将抓好支部学习、制度建设、完善基层党组织建设，争创学习型、制度型、服务型支部，发挥党支部战斗堡垒和党员先锋模范作用。
-- 大会宣布换届选举圆满结束，全体起立奏国际歌。
-## 结论与决定
-- 通过上届支部委员会工作报告。
-- 通过党员大会选举办法。
-- 通过支委候选人名单：卢燕娇、辛东升、杜军强、秦磊。
-- 通过监票人贾淑玲、计票人黄婷丽、刘彩云。
-- 选举卢艳娇、辛东升、杜军强为新一届支部委员会委员。
-- 选举卢艳娇为新一届党支部书记。
-- 分工：辛东升负责组织宣传工作，杜军强负责纪检工作。</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>8414/1655</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="13.5" customHeight="1" s="9">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:05
+  </si>
+  <si>
+    <t>发言人 1  00:00:05
 各位代表。现在我代表国务院向大会报告政府工作，请予审议，并请全国政协委员提出意见。2023年工作回顾，过去一年是全面贯彻党的二十大精神的开局之年，是本届政府依法履职的第一年。面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务。以习近平同志为核心的党中央团结带领全国各族人民顶住外部压力，克服内部困。
 发言人 1  00:01:00
 共同啊，付出艰辛努力，新冠疫情防控实现平稳转段。全年经济社会发展主要目标任务圆满完成。高质量发展，扎实推进社会大局保持稳定，全面建设社会主义现代化国家迈出坚实步伐。经济总体回升向好。国内生产总值超过126万亿元，增长5.2%，增速居世界主要经济体前列。城镇新增就业1244万人。
@@ -9661,73 +7529,9 @@
 我们要坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略。中国愿同国际社会一道落实全球发展战略。全球安全战略，全球文明战略，全球发展战，倡议全球安全战略，全球文明战略，推动构建人类命运共同体。各位代表，使命重在担当，奋斗创造未来，我们要更加紧密的团结在。
 发言人 1  00:51:00
 以习近平同志为核心的党中央周围，高举中国特色社会主义伟大旗帜，以习近平新时代中国特色社会主义思想为指导，坚定信心，开拓进取，努力完成全年经济社会发展目标任务。为以中国式现代化全面推进强国建设、民族复兴伟业不懈奋斗。</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>政府报告</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t># 2024年政府工作报告：稳中求进推动高质量发展
-## 报告概况
-2024年3月5日，国务院总理代表国务院向第十四届全国人民代表大会第二次会议作政府工作报告，提请大会审议，并请全国政协委员提出意见。报告全面回顾2023年工作成绩，明确提出2024年经济社会发展总体要求、主要预期目标和政策取向，系统部署全年政府工作任务。报告指出，2024年是中华人民共和国成立75周年，是实现"十四五"规划目标任务的关键一年，要坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，加快构建新发展格局，着力推动高质量发展，统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全，切实增强经济活力、防范化解风险、改善社会预期，巩固和增强经济回升向好态势，持续推动经济实现质的有效提升和量的合理增长，以中国式现代化全面推进强国建设、民族复兴伟业。2023年，面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务，全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元，增长5.2%，增速居世界主要经济体前列。
-## 核心政策
-- **2024年主要预期目标**：国内生产总值增长**5%左右**，城镇新增就业**1120万人**，城镇调查失业率**5.5%左右**，居民消费价格涨幅**3%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡，粮食产量**1.3万亿斤以上**，单位国内生产总值能耗降低**2.5%左右**，生态环境质量持续改善。
-- **积极的财政政策适度加力、提质增效**：赤字率拟按**3%**安排，赤字规模**4.06万亿元**；一般公共预算支出规模**28.5万亿元**；拟安排地方政府专项债券**3.9万亿元**；连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，今年先发行**10000亿元**。
-- **稳健的货币政策灵活适度、精准有效**：保持流动性合理充裕，促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。
-- **坚持稳中求进、以进促稳、先立后破**：多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施。
-- **全面取消制造业领域外资准入限制措施**：放宽电信、医疗等服务业市场准入，推动高质量共建"一带一路"走深走实。
-- **启动第二轮土地承包到期后再延长30年整省试点**：严守耕地红线，稳定粮食播种面积，扎实推进乡村全面振兴。
-## 重点工作
-### 1. 现代化产业体系建设
-- **推动产业链供应链优化升级**：实施制造业重点产业链高质量发展行动，促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划。
-- **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，开展"人工智能+"行动，实施制造业数字化转型行动。
-### 2. 科教兴国战略
-- **加强高质量教育体系建设**：制定实施教育强国建设规划纲要。
-- **加快推动高水平科技自立自强**：强化基础研究系统布局，推进关键核心技术协同攻关。
-- **全方位培养用好人才**：加大对青年科技人才支持力度。
-### 3. 扩大国内需求
-- **促进消费稳定增长**：培育壮大新型消费，稳定和扩大传统消费，鼓励和推动消费品以旧换新。
-- **积极扩大有效投资**：发挥政府投资带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳等领域，着力稳定扩大民间投资。
-### 4. 深化改革
-- **激发各类经营主体活力**：深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措。
-- **加快全国统一大市场建设**：谋划新一轮财税体制改革。
-### 5. 扩大高水平对外开放
-- **推动外贸稳规模优结构**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入。
-- **推动高质量共建"一带一路"走深走实**：深入实施自贸试验区提升战略。
-### 6. 统筹发展和安全
-- **稳妥有序处置风险隐患**：优化房地产政策，统筹好地方债务风险化解和稳定发展，加快构建房地产发展新模式。
-- **加强重点领域安全能力建设**：提升产业链供应链自主可控能力。
-### 7. "三农"工作
-- **加强粮食和重要农产品稳产保供**：严守耕地红线，提高高标准农田建设投资补助水平。
-- **扎实推进乡村全面振兴**：启动第二轮土地承包到期后再延长30年整省试点。
-### 8. 城乡融合和区域协调发展
-- **积极推进新型城镇化**：深化户籍制度改革，常住人口城镇化率已提高到66.2%。
-- **深入实施区域重大战略**：推动城乡融合和区域协调发展。
-### 9. 生态文明建设
-- **协同推进降碳、减污、扩绿、增长**：积极稳妥推进碳达峰碳中和，扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系。
-### 10. 民生保障
-- **多措并举稳就业促增收**：预计今年高校毕业生超过**1170万人**，强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作。
-- **提高医疗卫生服务能力**：居民医保人均财政补助标准提高**30元**，深化公立医院改革，引导优质医疗资源下沉基层。
-- **加强社会保障**：城乡居民基础养老金月最低标准提高**20元**，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全分层分类的社会救助体系。
-- **维护国家安全和社会稳定**：建设更高水平的平安中国。</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>9903/2349</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="13.5" customHeight="1" s="9">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:16
+  </si>
+  <si>
+    <t>发言人 1  00:00:16
 嗯。我们的节目正在通过b站微博和抖音同步推出，如果您在观看的过程中有任何的问题，都可以用不同的方式在我们的弹幕区进行留言，稍后呢也会有今天的嘉宾的点评答疑解惑，为了帮助广大考生全面了解2026年。研究生的招生情况，今天全天来到我们直播间的是杭州医学院。本场直播呢是杭州医学院检验医学院、生物工程学院的专场，那么今天也特地的邀请到了学校的一位中。
 发言人 1  00:01:00
 让我们的嘉宾来做客我们直播间，那么就是来自杭州医学院检验医学院生物工程学院党委书记。副院长宋宋宝峰副教授。主持人你好。
@@ -10545,78 +8349,9 @@
 也要感谢到场的呃宋书记带来的精彩的直播，啊，那么如果说前面的直播没有看到的同学呢，也没有关系啊，我们在本场直播的结束以后的24小时之内呢，就会将我们的回回看上传到 B 站，所以也是欢迎我们的考生能够随时来搜索。我们的本场的直播内容，那么如果说想要了解更多的报考信息呢，可以持续关注杭州医学院的官网和杭州医学院的官网，那么我们本场直播到这里就要结束了，各位考生，各位家长再见。
 发言人 2  00:57:53
 再见再见。好。</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>沟通交流会</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t># 杭州医学院医学技术专业硕士点2026年招考宣讲会纪要
-## 沟通背景
-杭州医学院检验医学院、生物工程学院党委书记、副院长宋宝峰副教授做客直播间，面向2026年考研考生及家长全面介绍医学技术专业硕士点的总体情况。该学位点于2024年获批，由检验医学院、生物工程学院（合署办公）作为组建学院，联合医学影像学院、康复学院、信息工程学院等5个学院共建，聚焦检验技术、医学影像技术、康复治疗、智能医学工程4个专业方向。2025年为首届招生，共录取64名考生。医学技术学科于2023年获批浙江省一流学科B类，近五年获国家级基金项目19项、纵向科研经费1300万元、横向合作课题经费2200余万元，获省科技进步一等奖2项，建成国家级一流本科课程2门、国家级一流本科专业建设点2个及多个省级科研平台。宋宝峰书记系统介绍了各方向学科优势、师资力量、培养方案与就业前景，并公布2026年招考计划与考试政策，现场解答考生关于就业前景、跨专业报考、暑期备考等疑问，整体沟通基调务实、信息充分，旨在吸引考生报考。
-## 核心信息
-### 1. 学位点基本架构与招生数据
-- **学位点架构**：医学技术专业硕士点于2024年获批，由5个学院共建，检验医学院、生物工程学院合署办公为组建学院，医学影像学院、康复学院、信息工程学院为共建学院。
-- **专业方向**：聚焦4个方向，即检验技术（细分为医检和卫检）、医学影像技术、康复治疗、智能医学工程。
-- **2025年招生**：首届录取64人，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
-- **学科建设**：2023年获批浙江省一流学科B类；近五年获国家级基金项目19项、省鉴定领先项目1项，纵向科研经费1300万元，横向合作课题经费2200余万元。
-- **科研成果**：获省科技进步一等奖2项、二等奖1项、三等奖2项；建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
-- **科研平台**：建有省生物标志物与器官诊断转化重点实验室（2024年）、检验诊断关键技术研究室（2022年）、康复模块和机器人国际联合实验室（2023年）、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、浙江省神经系统疾病数字化装备研发重点实验室（2024年）等省级平台。
-### 2. 各方向学科优势与负责人
-- **体外诊断领域**：优势显著，疫情期间与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册。
-- **医学影像技术方向**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势，拥有国家级本科专业建设点、省医学重点学科、省临床放射质控中心、国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地等平台。
-- **康复治疗方向**：依托省人民医院康复医学科，为省内综合医院中建科最早、人才最齐、技术最先进、设备最先进、社会效益最佳的康复医学科之一。
-- **智能医学工程方向**：聚焦阿尔茨海默病智能预警数字生物标志物，居国际领跑水平，为浙江省中医药重点学科、智能医学前沿交叉学院。
-- **方向负责人**：医学检验技术方向负责人吕建新教授，研究方向涵盖重大疾病新型生物标志物筛选及机制、新发突发传染病生物标志物及致病机制等，团队发表高水平论文200多篇，获省科技一等奖3项；卫生检验检疫方向负责人金大志教授，研究方向涵盖新发突发传染病病原体检测检验新技术、艰难梭菌致病机制与耐药机制等，团队发表SCI论文50多篇，参编专著6部；医学影像技术方向负责人徐秀芳教授，研究方向涵盖多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术等；康复治疗方向负责人倪湘明教授（附属人民医院），研究方向涵盖康复技术研发、神经损伤修复与再生、意识障碍促醒机制等，谢夏明教授团队获国家级课题23项、省级课题23项，国家发明专利和实用新型专利77项；智能医学工程方向负责人李凯教授，研究方向涵盖脑认知与脑疾病智能诊疗及康复、脑机接口高端数字医疗器械等。
-### 3. 师资队伍
-- **师资规模**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，其中正高35人，博士46人。
-- **人才称号**：教育部医学技术类专业教学指导委员会委员、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。
-- **领军人物**：吕建新教授为国家百千万人才工程人选、省万人计划领军人才、国家自然基金会医学技术检验学科专家组长；徐秀芳教授为省高校中青年学科带头人、研究生院院长兼医学影像学院院长、国家一流本科专业建设点医学影像技术专业负责人；叶祥明教授为省人民医院主任医师、二级教授、省康复学院院长、省卫生领军人才，主持国家级课题3项、省重大课题2项，发表SCI论文98篇；金大志研究员为美国华盛顿大学博士后、检验医学院学术院长、省生物标志物体外诊断转化重点实验室主任，主持国家级及省部级重大项目共25项；李凯教授为复旦大学公共卫生学院博士、信息工程学院院长、智能医学前沿交叉学科研究院执行院长。
-### 4. 硕士培养与毕业去向
-- **培养目标**：面向健康中国发展需要，服务区域行业产业发展，培养熟练掌握医学技术领域专业知识技能、具有创新实践能力的高层次应用型人才。
-- **培养方式**：教学、专业实践与学位论文相结合；全日制专业学位学制三年，最长不超过五年。
-- **学分要求**：毕业前学业课程不少于24学分，其中专业必修课分方向要求≥12学分，专业选修课需达到5-6个学分以上。
-- **培养环节**：第二学期开题，第三、第四学期（研二）过程性考核，研一第二学期进行学位论文答辩。
-- **就业方向**：医院相关科室（检验科、输血科、病理科、放射科、超声科、康复医学科、骨科、神经科、运动医学科等）、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等。
-### 5. 2026年招考政策
-- **招生计划**：2026年计划招生34人，仅供参考，以教育部正式下达人数为准。
-- **初试科目**：思想政治理论、英语（统考）加一门专业课（按方向自主命题）：检验考检验综合、影像技术考医学影像技术综合、康复治疗考康复治疗综合、智能医学工程考智能医学工程综合。
-- **检验综合内容**：分子生物学检验占40%、生物化学检验占30%、微生物学检验占30%；专业课分值300分，考试时长180分钟。
-- **复试政策**：目前以线下为主；复试成绩占比为初试60%、复试40%；复试内容中英语能力测试占20%、专业能力测试占40%、综合能力测试占40%。
-- **官方渠道**：杭州医学院研究生招生网（研究生招生.杭州医学院.教育.cn）、杭州医学院研究生教育微信公众号。
-## 各方诉求
-- **宋宝峰书记（主讲人）**：核心诉求是全面展示学位点学科优势、师资力量与培养成果，吸引优质考生报考；强调就业面广、有竞争力，可继续深造读博或进入三甲医院、疾控中心、医药企业等，并明确允许非本专业考生跨专业报考。
-- **2026年考研考生及家长（受众）**：核心关切集中在就业前景、复试环节构成与占比、暑期备考策略、跨专业报考可行性等方面；宋宝峰逐一回应，给出具体备考建议（英语做真题、思政关注时事、专业课聚焦官方大纲和参考书）。
-- **杭州医学院研究生招生部门**：负责发布招生计划、初试科目与考试大纲、复试办法等官方信息，具体招生人数以教育部正式下达为准，考生须通过官方渠道获取最新信息。
-## 沟通结果
-**达成共识**
-- **2026年招生计划**：医学技术专业硕士点计划招生34人，实际人数以教育部正式下达为准。
-- **初试科目设置**：思想政治理论、英语（统考）加一门专业课，专业课按方向自主命题。
-- **复试成绩构成**：初试占60%、复试占40%；复试内容中英语能力测试占20%、专业能力测试占40%、综合能力测试占40%。
-- **跨专业报考**：允许非本专业考生跨专业报考医学技术专业，如从事检验的可以报考检验方向。
-- **信息获取渠道**：考生应关注杭州医学院研究生招生网和研究生教育微信公众号获取最新信息。
-**待协调事项**
-- **招生计划确认**：2026年实际招生人数以教育部正式下达为准，学校将据此调整并发布最终计划。
-- **官方信息发布**：杭州医学院研究生招生部门负责发布初试科目与考试大纲、复试办法等官方信息，考生须持续关注官方渠道。
-- **直播回放**：宣讲会直播回放将在24小时内上传至B站，供考生及家长回看。</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>101.2</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>23026/3607</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="13.5" customHeight="1" s="9">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:13
+  </si>
+  <si>
+    <t>发言人 1  00:00:13
 好，那我们现在就上课了，那我们先思考一下，我们作为一个小部门，首先呢。观点。
 发言人 2  00:00:31
 对。
@@ -11156,61 +8891,9 @@
 是的。
 发言人 1  00:33:53
 想一下啊，好，我们先把这个先思考一下，我们做一个小图啊，涉及到我们的电视。</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>课堂记录</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t># 历史小论文写作规范与题型解题方法指导
-## 课程概况
-本次课程为历史学科小论文写作指导课，主讲教师围绕历史小论文的写作方法展开系统讲解。课程核心目标在于帮助学生掌握小论文写作的基本规范与各类题型的解题方法，提升观点提炼与论证能力。主讲人首先强调小论文写作的核心要求：观点必须明确，不能只是简单陈述形式，必须亮出观点并具有凝聚力；论证部分建议写2-3条支撑论据，不宜过多或过少；结构可按时间顺序或国内外等逻辑清晰罗列，结尾需总结升华，不能简单重复观点。随后，课程分类介绍了自命题、观点提示类、图表信息类三种题型，分别讲解解题步骤与注意事项。自命题类需按审题、读材料、控制篇幅的步骤推进；观点提示类需先列出观点、选择核心观点并明确判断，不能照抄材料；图表信息类需快速查看题头与横向纵向信息，注意信息间关系变化。课程通过武汉长江大桥、梁启超观点、历代民德变化等例题，逐一分析学生作答，指出审题、材料解读、观点提炼与升华等环节的常见问题，并给出改进建议。
-## 核心知识点
-### 1. 小论文写作基本要求
-- **观点明确**：核心是亮出观点并具有凝聚力，不能只是简单陈述形式。
-- **论证支撑**：论证部分建议写2-3条，不宜过多或过少，需有足够材料支撑。
-- **结构清晰**：可按时间顺序（如700时期、明清时期）或国内外等逻辑清晰罗列。
-- **总结升华**：结尾需进行总结升华，不能简单重复观点。
-### 2. 自命题类题型解题步骤
-- **审题**：注意要求中的"小红帽"和形成标准，明确题目指向。
-- **读材料**：抓主要信息并细看关系，理解材料内部逻辑。
-- **控制篇幅**：先写题目再罗列事实，确保与材料相关。
-- **例题分析**：通过武汉长江大桥例题，指出学生作答中审题不清、观点不明确等问题，强调要结合时代背景理解材料意图。
-### 3. 观点提示类题型分析
-- **列出观点**：先列出观点，选择核心观点并明确判断，不能照抄材料。
-- **结合时代背景**：通过梁启超观点例题，强调要结合时代背景（如1940年抗战时期）理解材料意图。
-- **注意关联**：注意观点与材料的关联性，避免脱离材料空谈。
-### 4. 图表信息类题型分析
-- **快速查看关键信息**：关注题头、横向纵向信息，把握图表整体框架。
-- **注意信息间关系变化**：提取有效信息进行分析，关注数据或内容的变化趋势。
-- **例题分析**：通过历代民德变化图表例题，引导学生思考春秋、东汉、宋明等不同时期民德水平与政治、社会状态的关系，并对比官方答案。
-## 问答记录
-- **论证部分写几条合适**：建议写2-3条支撑论据，不宜过多或过少，需有足够材料支撑。
-- **小论文结尾如何写**：需进行总结升华，不能简单重复观点。
-- **自命题类题型如何审题**：注意要求中的"小红帽"和形成标准，明确题目指向后再读材料。
-- **观点提示类能否照抄材料观点**：不能照抄材料，需先列出观点、选择核心观点并明确判断。
-- **图表信息类如何快速提取信息**：快速查看题头、横向纵向信息，注意信息间关系变化，提取有效信息进行分析。
-## 课后任务
-- **课后作业**：针对自命题类题型，按照审题、读材料、控制篇幅的步骤进行练习，注意审题中的"小红帽"要求，先写题目再罗列与材料相关的事实。
-- **复习重点**：掌握小论文写作基本要求（观点明确、论证2-3条、结构清晰、结尾升华）；复习观点提示类题型，练习列出观点、选择核心观点并明确判断，避免照抄材料，结合时代背景理解材料意图；复习图表信息类题型，练习快速查看图表关键信息（题头、横向纵向），注意信息间关系变化，提取有效信息进行分析。</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>12357/1559</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="13.5" customHeight="1" s="9">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:01:21
+  </si>
+  <si>
+    <t>发言人 1  00:01:21
 各位代表。第14届全国人民代表大会第三次会议。出席代表2929人。今天的会议出席2880人，缺席49人，出席人数符合法定人数。现在我宣布，中华人民共和国第十四届全国人民代表大会第三次会议开幕。请全体起立，
 发言人 2  00:02:10
 唱国歌。
@@ -11350,63 +9033,9 @@
 各位代表，信心凝聚力量，实干谱写华章，我们要更加紧密的团结在以习近平同志为核心的党中央周围，高举中国特色社会主义伟大旗帜，以习近平新时代中国特色社会主义思想为指导，迎难而上，锐意。进取，努力完成全年经济社会发展目标任务，确保十四五规划圆满收官，为以中国式。
 发言人 2  00:49:00
 现代化，全面推进强国建设，民族复兴伟业，不懈奋斗。</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>政府报告</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t># 十四届全国人大三次会议开幕 李强作政府工作报告
-## 报告概况
-第十四届全国人民代表大会第三次会议于2025年3月5日在北京开幕，出席代表2880人，符合法定人数。国务院总理李强代表国务院向大会作政府工作报告，回顾2024年工作，提出2025年经济社会发展主要预期目标，并部署全年政府工作重点任务。报告指出，2024年面对外部压力加大、内部困难增多的复杂严峻形势，经济运行总体平稳、稳中有进，全年经济社会发展主要目标任务顺利完成，国内生产总值达到134.9万亿元，增长5%。报告强调，2025年坚持稳中求进工作总基调，实施更加积极的财政政策和适度宽松的货币政策，大力提振消费、因地制宜发展新质生产力、深入实施科教兴国战略，确保"十四五"规划圆满收官，并启动"十五五"规划编制工作。
-## 核心政策
-- **2025年经济社会发展主要预期目标**：国内生产总值增长5%左右，城镇调查失业率5.5%左右，城镇新增就业1200万人以上，居民消费价格涨幅2%左右，居民收入增长和经济增长同步，国际收支保持基本平衡，粮食产量1.4万亿斤左右，单位国内生产总值能耗降低3%左右，生态环境质量持续改善。
-- **更加积极的财政政策**：赤字率拟按4%左右安排，赤字规模5.66万亿元；拟发行超长期特别国债1.3万亿元，发行特别国债5000亿元支持国有大型商业银行补充资本；安排地方政府专项债券4.4万亿元，合计新增政府债务总规模11.86万亿元，比上一年增加2.9万亿元。
-- **适度宽松的货币政策**：适时降准降息，保持流动性充裕，推动社会综合融资成本下降。
-- **大力提振消费**：安排超长期特别国债3000亿元支持消费品以旧换新，中央预算内投资已安排7350亿元。
-- **保障和改善民生**：城乡居民基础养老金最低标准再提高20元；制定促进生育政策，发放育儿补贴。
-## 重点工作
-### 大力提振消费、提高投资效益
-- **消费品以旧换新**：安排超长期特别国债3000亿元支持消费品以旧换新，扩大内需规模。
-- **扩大有效投资**：中央预算内投资已安排7350亿元，发挥政府投资带动作用。
-### 因地制宜发展新质生产力
-- **培育未来产业**：培育生物制造、量子科技、具身智能、6G等未来产业，推动科技创新和产业创新融合发展。
-### 深入实施科教兴国战略
-- **教育强国建设**：制定实施教育强国建设三年行动计划，逐步推行免费学前教育，提升教育公共服务质量。
-### 推动标志性改革举措加快落地
-- **零基预算改革**：开展中央部门零基预算改革试点，提高财政资金使用效益。
-### 扩大高水平对外开放
-- **扩大开放试点**：扩大电信、医疗、教育等领域开放试点，稳步扩大制度型开放。
-### 有效防范化解重点领域风险
-- **房地产与地方债务风险化解**：推动房地产市场止跌回稳，稳妥化解地方政府债务风险，守住不发生系统性风险底线。
-### 着力抓好"三农"工作
-- **粮食安全与乡村振兴**：稳定粮食播种面积，巩固拓展脱贫攻坚成果，推进乡村全面振兴。
-### 推进新型城镇化和区域协调发展
-- **新型城镇化战略**：深入实施新型城镇化战略行动，常住人口城镇化率持续提升，促进区域协调发展。
-### 协同推进降碳、减污、扩绿、增长
-- **绿色低碳转型**：积极稳妥推进碳达峰碳中和，持续降低单位国内生产总值能耗，改善生态环境质量。
-### 加大保障和改善民生力度
-- **养老保障**：城乡居民基础养老金最低标准再提高20元，增强老年人生活保障。
-- **生育支持**：制定促进生育政策，发放育儿补贴，降低家庭养育成本。
-- **规划编制**：今年将开展"十五五"规划编制工作，为中长期发展谋篇布局。</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>10273/1588</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="13.5" customHeight="1" s="9">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:10
+  </si>
+  <si>
+    <t>发言人 1  00:00:10
 各位业主大家各位专家大家好，就是说大家有什么疑问的话呢可以来提问。我来这个答疑，谢谢大家。
 发言人 2  00:00:31
 我这里有几个问题啊，呃第一
@@ -11602,109 +9231,9 @@
 不知道吧？你说。
 发言人 2  00:35:33
 本第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源新东源物业管理有限公司54.48分。那么通过我们今天的评标，呃第一名。正标人，候选人为呃深圳市资平物业发展有限公司，提交完毕。好，那么恭喜我们的深圳市林业发展有限公司今天的招标活动圆满结束，谢谢大家。</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议为景城苑小区物业管理服务招标的评标与答疑环节，由业委会代表主持，长沙富佳物业与深圳市资平物业两家公司先后接受提问并阐述服务方案。评标委员会在全程保密、暂停网络直播、录像材料不予公开的条件下进行打分，评分规则为去掉一个最高分和一个最低分。最终，深圳市资平物业发展有限公司以最高分中标，长沙富佳物业得72.91分，湖南恒居基业物业得60.73分，重庆新东源物业得54.48分。长沙富佳物业在答疑中承诺一年内完成标书所列12大改造项目，并针对停车管理、承接查验、安防升级等提出具体措施。深圳市资平物业在陈述中强调财务透明、管理透明、团队直招，并提出针对老旧项目的四步改造计划，承诺进场第一个月集中整改环境绿化，半年内完成设备设施排查与整改，八个月内实现项目有效运作，一年内达到有序状态。两家公司均就承接查验、安防停车、楼层杂物等问题作出回应，最终资平物业以更具体的方案获得评标委员会认可。
-## 要点梳理
-### 1. 富佳物业答疑：改造计划与时间
-- 业委会代表首先就富佳物业中标后的改造计划提问，富佳物业回应称具体改造项目已在标书117页详细说明，预计一年内完成。
-- 改造项目共12大项，详见标书117页。
-### 2. 富佳物业答疑：停车管理问题
-- 业委会指出小区存在车辆停放不规范、电动车乱停现象，富佳物业分析原因并提出针对性措施。
-- 富佳物业将分析乱停原因（场地不足、距离远、不自觉等），制定不同对策。
- - 若停车位不够则增加停车位。
- - 若业主不自觉则派保安、客服现场说服劝阻纠正。
-### 3. 富佳物业答疑：承接查验与交接
-- 业委会询问中标后如何与原物业进行承接查验及应对交接不畅，富佳物业介绍其丰富经验与具体安排。
-- 富佳物业提前两周安排项目负责人入场摸底，提前一周安排服务人员到位并培训。
-- 交接不顺利时先与原物业私下沟通，无法解决则请业委会或街道社区协调，必要时在许可下采取强制措施。
-### 4. 富佳物业答疑：安防与停车管理改善
-- 业委会提出小区监控门禁失效、停车混乱问题，富佳物业提出五项具体改善措施。
-- 大门口增设人行门禁系统，支持手机微信、卡、密码进出。
-- 升级大堂报到系统，录入业主车辆信息，临时车辆登记放行。
-- 地面增设隔离墩，禁止公共场所停车，保障消防通道畅通。
-- 建设外围停车场并安装停车管理系统。
-- 增设电动车停车场，解决乱停乱放问题。
-### 5. 富佳物业答疑：类似项目管理经验与满意度措施
-- 业委会询问富佳物业是否有类似小区管理经验及提升满意度、收费率的措施。
-- 富佳物业表示没有与景城苑完全相似的小区，但采取四句话原则：用心倾听、如实记录、马上处理、及时反馈。
-### 6. 资平物业陈述：公司概况与服务理念
-- 资平物业代表介绍公司背景、业委会项目经验及服务理念，强调财务透明和管理透明。
-- 资平物业成立于2004年，总部在深圳，全国有367个项目，其中127个为业委会项目。
-- 公司创始人陈志平为万科物业创始人，参与建立中国第一个业委会。
-- 资平物业为中国物业管理协会副会长单位、全国百强企业。
-- 承诺财务透明，每季度公示物业管理费、停车费等财务信息。
-- 团队编制16人，薪酬福利高于同类周边项目，一线人员不外包。
-### 7. 资平物业陈述：四步改造计划
-- 资平物业提出针对老旧项目的四步改造计划，明确时间节点与资源调配。
-- 第一步"洗理静音"：进场第一个月调动湖南战队资源，全面清扫环境绿化，保证感官干净整洁有序。
-- 第二步"疏金活选"：调动集团设备公司工程师，全面排查诊断设备设施，合理范围内集中改造。
-- 第三步"疑难杂症"：涉及重大改造（消防、渗水等）需业委会授权或业主大会招投标，八个月内完成。
-- 第四步"有效提升"：导入公司管理标准与经验，延续至项目。
-### 8. 资平物业陈述：特色服务与社区文化
-- 资平物业介绍将导入顾客管理系统、大数据管理及社区文化活动，提升服务品质。
-- 导入顾客管理系统，集中处理业主投诉、咨询、报事，确保有人跟进回访。
-- 根据大数据分析业主投诉，指导下月工作重点。
-- 针对老龄化开展社区活动，如教老年人使用抖音，每两个月开展一次社区文化活动。
-### 9. 资平物业答疑：改造措施与时间
-- 业委会重复提问改造措施与时间，资平物业结合勘察结果给出具体安排。
-- 进场第一个月集中整改环境绿化、楼道杂物、牛皮癣等，保证基本面干净整洁有序。
-- 半年内完成设备设施排查与整改，八个月内实现项目有效运作，一年内达到有序状态。
-### 10. 资平物业答疑：包干制经验与公益服务
-- 业委会询问包干制经验及公益服务，资平物业强调财务透明、团队直招，并介绍长沙项目中的公益服务。
-- 资平物业在长沙有11个项目，其中10个为包干制，1个为酬金制。
-- 包干制下同样保证财务透明、管理透明，团队直招，管理干部30%来自现有优秀员工，60%左右重新招聘。
-- 长沙项目提供居家上门服务，员工免费，材料费业主自付；提供24小时业主护送服务等。
-### 11. 资平物业答疑：承接查验与交接
-- 业委会询问承接查验安排，资平物业强调前期准备、专业分组及集团资源支持。
-- 前期与社区街道、派出所、原物业、业委会沟通，明确设备设施、债务债权。
-- 按专业线分组，委派集团工程师协助查验，避免遗留问题。
-- 承接查验期间增派150%人员，现有16人团队扩充。
-### 12. 资平物业答疑：安防与停车管理
-- 业委会提出监控门禁失效、停车混乱问题，资平物业提出人员管控、停车方案与技术升级。
-- 关键岗位（门岗、门勤岗、车务）由老员工担任，确保责任心。
-- 收集业主车辆信息，制定停车管理方案，包括禁区停放、动线规划。
-- 升级道闸系统，识别外来车辆；利用设备公司技术手段加强监控。
-### 13. 资平物业答疑：楼层杂物与晾晒问题
-- 业委会询问如何在不激发矛盾的前提下解决楼层顶层杂物与乱搭乱晒，资平物业提出疏导为主、强制为辅的策略。
-- 宣传引导，普及法律知识，让业主明白堆放杂物的风险与法律责任。
-- 与社区、应急管理部门联合行动，上门沟通，给予处理时限。
-- 提供临时存放区域，但限期解决。
-- 设置集中晾晒区，物业可提供免费上门晾晒服务。
-### 14. 评标与结果公布
-- 所有答辩结束后，评标委员会进行打分，去掉最高最低分，最终公布中标结果。
-- 打分环节全程保密，暂停网络直播，录像材料不予公开。
-- 评分规则：去掉一个最高分和一个最低分。
-- 最终得分：长沙富佳物业72.91分，湖南恒居基业物业60.73分，重庆新东源物业54.48分。
-- 第一名中标候选人为深圳市资平物业发展有限公司。
-## 结论与决定
-- **中标结果**：深圳市资平物业发展有限公司中标景城苑小区物业管理项目。
-- **评分规则**：评标打分规则为去掉一个最高分和一个最低分。
-- **保密要求**：打分环节全程保密，暂停网络直播，录像材料不予公开。</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>11743/2938</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="13.5" customHeight="1" s="9">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:05
+  </si>
+  <si>
+    <t>发言人 1  00:00:05
 三观正直一把尺，扎扎实实讲历史。我是李正，欢迎来到正直讲史。我们本期要讲的人是康熙朝文渊阁大学士陈廷敬。在康熙王朝的影视剧中啊，比起党同伐异的索额图与明珠，陈廷敬仿佛永远忠诚老练。在影视剧中，他既支持撤藩，又毛遂自荐招抚台湾，甚至征剿格尔丹时，他还全力维护过康熙的后勤粮草。
 发言人 1  00:00:29
 不过我们要说以上这些事，历史上的陈廷敬都没有做过。但这并不是说陈廷敬他不重要，恰恰相反，历史上的陈廷敬直到临终前，康熙依然在询问着他说，朕的大臣中是否还有其他像你一样的人。康熙的原话叫，朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？
@@ -11810,61 +9339,9 @@
 像《论语》中讲，叫苟正其身矣，于从政乎何有？意思说一个人只要自身品。行端正，那么治理正义就没有什么是困难的。那这句话或许是陈廷敬在3岁时就听他妈妈张氏讲过，可陈廷敬帅就帅在他儿时学过的那些道理，直到死他都没有违背过。好了，那关于陈廷敬的故事我们就讲到这里吧，内容可能有些琐碎和平淡，没有大开大合的那些波澜壮阔的事情，也不知道有多少小伙伴会一直看到最后啊，那也希望看到最后的小伙伴能给 up 来个一键三连，这是对我更新的最大鼓励。
 发言人 1  00:25:31
 感谢感谢。另外想了解更多。</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>专题讲座</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t># 康熙朝文渊阁大学士陈廷敬生平述评
-## 讲座概况
-本期视频由主讲人李正（正直讲史）讲述康熙朝文渊阁大学士陈廷敬的一生，旨在澄清影视剧虚构，展现其真实历史功绩与品格。陈廷敬本名陈敬，字子端，号午亭，1638年（崇祯11年）生于山西泽州府阳城县，家族六代读书人。其母张氏自幼随父张弘毅研读儒家经典与《资治通鉴》，婚后勤学不辍，亲自为陈廷敬开蒙。陈廷敬6岁前已由母亲口授背完《论语》《孟子》《大学》《中庸》《诗经》，9岁作《咏牡丹》获母亲盛赞。顺治八年（1651年）14岁以童子第一入州学，20岁中举，21岁中进士入翰林院任庶吉士。因与直隶陈敬重名，主动上书改名，顺治赐名廷敬。顺治18年庶吉士毕业考试考取同届第一，授秘书院检讨。同年顺治驾崩，康熙元年母亲病倒，陈廷敬请假归乡三年。康熙六年（1667年）考察一等称职，此后历任国子监司业、日讲起居注官、经筵讲官、翰林院掌院学士、左都御史及工户吏三部尚书，康熙42年升任文渊阁大学士，总理南书房事务。晚年多次请退，康熙49年第四次请退获准，两年后病逝，终年75岁，谥号文贞。
-## 核心观点
-### 妈妈张氏的开蒙
-- **书香门第，母教开蒙**：陈廷敬家族往上数六代都是读书人，父亲陈长七为管理家业未走仕途，但入选顺治朝国子监。母亲张氏自幼随父张弘毅读书，学习四子书、通鉴及列女传，婚后仍勤学不辍，亲自为陈廷敬开蒙。
-- **早慧成才，少年得志**：陈廷敬6岁外出上学前已由母亲口授背完《论语》《孟子》《大学》《中庸》《诗经》，9岁作诗咏牡丹，母亲夸其天才。顺治八年（1651年）14岁以童子第一入州学，20岁中举人，21岁中进士，同年入选翰林院任庶吉士。
-- **同名受牵连，主动改名**：顺治15年四月，顺治检阅考试，取马进勇、杨正中、山西泽州人陈敬、直隶通州人陈敬等32人为庶吉士。直隶陈敬因清书未习熟被顺治点名批评并罚俸一年，陈廷敬因同名受牵连，主动上书改名，顺治赐名廷敬。
-- **毕业夺魁，归乡守孝**：顺治18年庶吉士毕业考试，陈廷敬考同届第一，获授秘书院检讨。同年年初顺治驾崩；康熙元年母亲病倒，陈廷敬请假归乡三年。
-### 圣祖康熙的讲师
-- **政绩卓著，整顿陋习**：康熙六年（1667年）陈廷敬考察一等称职，两年后升任正六品国子监司业，废除学生拜见需送礼的不成文规定，凡送礼者不见。
-- **朝夕讲学，风格外放**：康熙11年十月充日讲起居注官，时年35岁，与康熙朝夕相处4年；康熙15年九月充经筵讲官，时年39岁。其教学风格外放，讲评经史狠辣，曾痛斥孙权背刺关羽为猪狗，原话："无鼠相存，譬犹唇齿，不必智者而知之。全记上书以讨荆州自效，明年全破斩云长传其手，全其屯权也哉。"
-- **执掌翰林，母丧获殊荣**：康熙16年正月任翰林院掌院学士，教习庶吉士。同年母亲张氏去世，终年59岁。康熙下令满汉大臣有丧，朝廷均派大臣祭奠，打破旧例；礼部以陈廷敬母亲封号按詹事品级不够资格反对，康熙坚持追封并按学士品级祭奠，并言："以平靖世将握秦而恩福待，吾何以劝劳臣乎？"
-### 至公无私的落幕
-- **监察外官，严查贪腐**：康熙20年陈廷敬守孝三年后重返官场，康熙23年47岁升任从一品左都御史，位列中央九卿。针对捐纳买官者，上奏要求上岗前追加考试，吏部以"以前补用人员从未考试"为由反对，康熙支持并补充要求各地督抚详查已任命官员，原话："临民之官，若不识字义，何以办理民事而尽职掌？此事着一意不分捐纳与不捐纳，凡临民之官内有不识字义者，着该督府不时实行查参修治。"此后严查各省督抚作风与赈灾懒政，亲自拟定新赈灾报批流程。
-- **亲家涉案，主动辞官**：康熙26年，湖广巡抚张谦（陈廷敬亲家）贪污被抓，供称贿赂陈廷敬等三人。康熙传旨主审官马齐："尔等亡神，此时需旧款需问，不可蔓延，若蔓延则千累者重，倘有别事，尔等既来密奏。"只处理张谦，不得株连。陈廷敬主动辞官，康熙准许但留京修书。
-- **复出掌部，位极人臣**：康熙29年53岁复出再任左都御史，此后历任一年刑部尚书、六年户部尚书、四年吏部尚书。康熙42年66岁升任文渊阁大学士，总理南书房事务。
-- **晚年请退，荣终谥文贞**：康熙46年起70岁开始申请退休，70岁、71岁、72岁连续三次申请均被康熙拒绝。康熙49年73岁第四次申请退休获准，康熙赐匾额"五亭山村"和楹联"春归乔木浓阴茂，秋到黄花晚"，并言："朕特殊匾联赐卿，自此不与人写字矣。"两年后陈廷敬病逝，终年75岁，谥号文贞。康熙包办治丧费用，从大内找紫砂碗做棺材，命各部院满汉大臣往吊。
-## 金句总结
-&gt; "自古未有不晓文艺之人可以为民父母者也，有未经考职遂行捐纳者，于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试。"
-&gt; —— **陈廷敬**（针对捐纳买官者，上奏要求上岗前追加考试）
-&gt; "临民之官，若不识字义，何以办理民事而尽职掌？此事着一意不分捐纳与不捐纳，凡临民之官内有不识字义者，着该督府不时实行查参修治。"
-&gt; —— **康熙**（支持陈廷敬对捐纳买官者追加考试的建议，并补充要求各地督抚详查已任命官员）
-&gt; "以平靖世将握秦而恩福待，吾何以劝劳臣乎？"
-&gt; —— **康熙**（驳回礼部反对意见，坚持追封陈廷敬母亲并按学士品级祭奠）
-&gt; "尔等亡神，此时需旧款需问，不可蔓延，若蔓延则千累者重，倘有别事，尔等既来密奏。"
-&gt; —— **康熙**（张谦案传旨主审官马齐，只处理张谦一人，不得扩大株连）
-&gt; "朕特殊匾联赐卿，自此不与人写字矣。"
-&gt; —— **康熙**（康熙49年准许陈廷敬第四次退休申请，赐匾额与楹联）
-## Q&amp;A 环节
-本次讲座以主旨分享为主，现场未设置问答互动。</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>9132/2371</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="13.5" customHeight="1" s="9">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:03
+  </si>
+  <si>
+    <t>发言人 1  00:00:03
 有的美感。
 发言人 2  00:00:05
 因为他是这样，就是中国的这个在宋明这两。
@@ -12468,72 +9945,9 @@
 我们。
 发言人 1  00:32:29
 强强3</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>采访记录</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t># 《锵锵三人行》畅谈日本文化精神与明朝历史兴亡
-## 访谈概述
-本期《锵锵三人行》邀请《明朝那些事儿》作者当年明月（石悦）与嘉宾马未都，围绕刚播完的日本历史剧《大奥》展开对日本文化、民族精神及中日文化差异的讨论，随后转入对明朝历史的深入探讨。主持人窦文涛开场感谢马未都引荐当年明月，并称赞《明朝那些事儿》写得好看、放松。嘉宾们一致认为《大奥》是继《大长今》之后更有影响的国外电视剧，制作精良，反映日本历史与文化。节目以轻松闲聊方式，穿插嘉宾个人经历与观点交锋，呈现对历史与文化的多元解读。围绕日本民族精神，当年明月提出极端精神说，马未都则强调忠诚文化与重视生命，二人就日本民族对生命的态度展开交锋。转入明朝话题后，当年明月分享创作初衷与明史研究难点，推崇朱元璋，并与马未都就英雄史观、历史教训的悖论展开讨论，兼及明代皇帝趣事、晚明市民生活与宋明审美变迁，呈现对历史与文化的多元解读。
-## 访谈详细记录
-### 1. 《大奥》观感与日本历史背景
-- **《大奥》的整体评价**：嘉宾们一致认为《大奥》是继《大长今》之后更有影响的国外电视剧，制作精良，反映日本历史与文化。
-- **当年明月的观感**：该剧吸引他的是严谨的精神，演员专业，场面华丽。
-- **《大奥》的历史对应**：三部曲中前两部对应中国晚清到清初时段，第三部在明治维新之前。
-- **马未都的补充**：《大奥》即日本的后宫，日语中“奥”指很深的地方，即屋子最里处。
-- **日本权力结构**：日本天皇一直是摆设，实际权力掌握在幕府将军手中；德川家康开创德川幕府后，日本所有权力集中在一人手上。天皇曾因没钱举办活动而向将军要钱未果，甚至以退位抗议。
-### 2. 日本文化与民族精神讨论
-- **极端精神说**：当年明月认为日本民族具有极端精神，追求把事情做到尽头。日本战后用30年时间成为世界第二经济强国（以绝对量计算）是必然，源于全民族的极端精神，且日本是世界上强国中唯一没有资源的国家。
-- **忠诚文化**：马未都强调日本是忠诚文化的典型国家，并举例日本豆腐行业规定当天做当天卖，工人夜里11:45等待，12点整开始干活；还有做绳子做到全日本第一的人，几年不赚钱先铺市场，后加价4%盈利。
-- **中日精神对比**：当年明月指出，中国文化精神是中庸，讲究融合；日本精神坚持一个原则，做到极致。
- - 当年明月认为日本民族有寻死的潜在欲望，藐视生命，看樱花只看落的那天，对死亡不惧怕甚至向往，二战暴行源于藐视生命。
- - 马未都持相反观点，认为日本民族不是藐视生命，而是重视生命资本，经济危机时很多身家万贯的人选择自杀是重视生命的表现。
-### 3. 明朝历史与明史研究
-- **创作初衷**：当年明月写明朝是因为明史资料最多，但一个事件可能有七个不同说法，研究难度大；历史研究有两个难点，一是先秦，二是明清。
-- **明朝历史的跌宕起伏**：马未都认为明朝260多年的过程本身跌宕起伏，如土木堡之变、夺门之变等，构成现代版电视剧般的离奇情节。
-- **朱元璋评价**：当年明月推崇朱元璋，认为他是历史上唯一由乞丐当上皇帝的人，刘邦好歹是村长；明朝的规章制度由朱元璋定下，基本没有太大改动。
- - 马未都认为人的因素最大，改变时势一定是出现一个人，朱元璋就是这样的英才。
- - 当年明月强调历史事件有背景，不能简单套用经验，提出历史教训的悖论，认为我们并不比前人聪明，史书只是照片，不是录像。
-### 4. 明朝兴亡与经验教训
-- **仁宣盛世**：马未都认为明朝有仁宣盛世，但时间太短不常提。
-- **晚明市民生活**：晚明时期市民生活轻松，江浙工商业兴起，出现三言二拍等市民小说；吴门画派如文徵明、唐寅等作品充满欣赏感，而八大山人朱耷的画作则反映对社会的不满。当年明月补充，明末很多真相被掩盖，市民生活特别轻松，想去哪就去哪，连皇册都不用了，给人打工活得很滋润。
-- **明朝灭亡的疑点**：1644年明朝灭亡时，北京可能发生瘟疫（疙瘩瘟，可能是天花）。
-- **王朝寿命规律**：马未都指出，中国历史上超过300年大限的王朝只有宋朝（南北宋接上），汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
-### 5. 明代皇帝趣事与审美变迁
-- **正德皇帝南巡风波**：明武宗正德皇帝要去江南，大臣跪在金水桥前抗议，锦衣卫打死十几人；正德皇帝被评价为明朝最荒淫的皇帝，但无后代，皇位由堂兄弟嘉靖继承。当年明月指出，明武宗实录是嘉靖指派杨廷和等人编的，可能有偏颇。
-- **天启皇帝的木匠爱好**：天启皇帝爱做木匠，干完活拆大盆去卖，卖完还打听销量；马未都认为这从侧面反映当时社会时尚，明式家具在国际上地位高绝非偶然。
-- **宋明与满族审美差异**：马未都认为宋明是典型的汉人政权，文人欣赏的审美比较高，对美的判断不是表象的；满族作为异族，对美的判断是表象的，今天凡是外在直观能看到的都卖得贵，而100年前值钱的一定是素雅的。
-## 金句总结
-&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
-&gt; —— **当年明月**（回应历史教训能否直接套用于现实的问题，提出历史教训的悖论）
-&gt; “他是完全每个人发自内心的，就是我们有时候去看看一个看一个事物。”
-&gt; —— **当年明月**（解释日本民族极端精神源于全民族发自内心的自觉，而非外在强制）
-&gt; “我觉得日本民族他不是藐视生命，他是重视啊，他是翻着的。”
-&gt; —— **马未都**（回应当年明月关于日本民族藐视生命的观点，提出相反看法）
-&gt; “他对于死亡他……是应该说是有点向往的感觉，或者说不惧怕。”
-&gt; —— **当年明月**（阐述日本民族对死亡的态度，认为其不惧怕甚至向往死亡）
-&gt; “我是认为人的因素最大，就是改变时势一定是出现一个人。”
-&gt; —— **马未都**（表达英雄史观，认为朱元璋这样的英才改变了时势）</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>17496/2457</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="13.5" customHeight="1" s="9">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:04
+  </si>
+  <si>
+    <t>发言人 1  00:00:04
 说当年的感觉已经远去，这是很痛苦的，我已经把那个40多最好的一段时间浪费了，就拖了2个多月，活着也蛮认真的。
 发言人 2  00:00:14
 我这还忍着。
@@ -12887,72 +10301,9 @@
 那也
 发言人 1  00:25:42
 那也是勉强吹进来的。假如那个历史的长河里边有一个主题的话，这个主题就是。一个一个世界，一个一个的人。是当年的感觉，这是很痛苦的。我已经把那个40多岁到50岁最好。</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>采访记录</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t># 余华访谈：文学创作阶段、批评应对与人生感悟
-## 访谈概述
-本次访谈围绕作家余华的文学创作历程、写作理念、个人经历与心态展开。余华以自学游泳的1.0至3.0版本类比文学创作，回顾了从逼自己坐下来写、到通过视觉行为表现心理描写、再到3.0版本后不再升级的三个重要时刻。他提到卡夫卡和威廉·福克纳对自己写作的启发，并坦言《活着》可能被视为4.0版本，但对他已不再是难题。余华还分享了《兄弟》《第七天》《文城》等作品的创作背景与批评应对，谈及被马尔克斯误导、调侃莫言在莎士比亚故居发誓，以及面对互联网时代个人言论被误传的态度。访谈最后，余华表达了对人生、中年危机的感悟，并希望以遗忘的姿态留在历史长河。
-## 访谈详细记录
-### 1. 文学创作阶段划分与写作理念
-- **三个重要时刻**：余华将文学创作划分为三个关键节点。第一个时刻是逼自己坐下来写，强调“让屁股和椅子建立友谊”，并指出幻想作品成功是支撑写作的动力；第二个时刻是心理描写通过视觉行为表现，他提到威廉·福克纳写穷白人杀富白人时“让心脏停止跳动，让眼睛睁开”的手法，以及鲁迅《狂人日记》中“赵家的狗看了我一眼”的视觉表达；第三个时刻是3.0版本之后写作已畅通无阻，不再升级。
-- **《活着》的定位**：余华表示《活着》可能被视为4.0版本，但对他已不再是难题。
-- **写作速度与运气**：余华提到《18岁》一天写完约6000字，并认为作家需要运气，什么时候写什么作品很重要。
-### 2. 作品创作背景与时代关系
-- **《兄弟》的创作历程**：创作始于1996年，2004年重新续写时发现时代变化更大，庆幸当年没有写完。余华认为中国始终处于大变化时代，作家需要与时代相遇并保持激情。
-- **创作状态的反思**：余华坦言最好的写作状态在40多岁到50岁，但那段时光被浪费，只出了两部作品。
-- **未完成的长篇小说**：2006年开始写一部长篇小说，实践跨度与《兄弟》相同，但未完成，因为“当年的感觉已经远去”。余华计划开学时与学生见面，处理学校事务后回三亚继续写作，希望找回感觉。
-### 3. 个人经历与人生感悟
-- **童年游泳经历**：余华分享童年游泳被海流带到40里外、赤脚走回天快亮的经历，以及第一次看到大海时感受到人生的宽广。
-- **三亚星空与月光**：他在三亚看到童年星空，通过月光发现月光是金色的。
-- **人生感受的转变**：余华认为人生就是宽广，小时候的人生感受是向前看，现在则是往后看，回忆占多了。
-- **中年危机与焦虑应对**：余华提到中年危机是现实世界每天重复，只有写作能带来新东西。对于年轻人的焦虑，他建议选择性地屏蔽负面消息，因为“我们可以选择什么让自己去知道，什么让自己去不知道”。
-### 4. 对批评的态度与自我调节
-- **《兄弟》遭遇批评**：出版时遭遇猛烈批评，余华最初努力解释，后来选择不看。
-- **区分有道理与无道理的批评**：批评宋凡平太完美没有道理，因为宋凡平是阶段性人物；但批评《第七天》中底层人物未必都善良有提醒作用。
-- **《第七天》出版应对**：只接受了一个采访，让朋友做好被骂的准备。
-- **想写喜剧**：余华坦言想写喜剧改变读者印象，因为“我的悲剧写的太重了”。
-### 5. 互联网时代与公众人物心态
-- **冷静期与误传**：余华曾有一年冷静期，停止所有活动和采访，但发现自媒体时代会翻出几十年前的事情，且互联网上关于他的话有一半不是他说的。
-- **不担心关注消散**：余华表示不担心公众关注消散，因为“我的工作是写作，不是说话”。
-### 6. 文学理想与历史姿态
-- **被马尔克斯误导**：余华认为被马尔克斯误导，不必在一本书里写一个世纪的故事。伟大的作家如托尔斯泰、狄更斯、莎士比亚等都没有这样做，马尔克斯能写是因为拉丁美洲的混乱世界。
-- **调侃莫言**：余华调侃莫言在莎士比亚故居发誓是瞎扯，提到三人一起买帽子。
-- **追求宽度而非高度**：余华表示不再追求高度，追求宽度，希望以遗忘的姿态留在历史长河。
-## 金句总结
-&gt; “让屁股和椅子建立友谊。”
-&gt; —— **余华**（谈文学创作的第一个重要时刻：逼自己坐下来写）
-&gt; “我的工作是写作，不是说话。”
-&gt; —— **余华**（回应不担心公众关注消散的原因）
-&gt; “我的悲剧写的太重了。”
-&gt; —— **余华**（解释想写喜剧改变读者印象的动机）
-&gt; “我们可以选择什么让自己去知道，什么让自己去不知道。”
-&gt; —— **余华**（建议年轻人面对焦虑时选择性屏蔽负面消息）
-&gt; “我们整整一代中国作家都想在一本书里边写那个一个世纪的故事，但是其实没有必要。”
-&gt; —— **余华**（谈被马尔克斯误导的反思）
-&gt; “当年的感觉已经远去。”
-&gt; —— **余华**（解释2006年开始的长篇小说未完成的原因）</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>11212/2042</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="13.5" customHeight="1" s="9">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 战役柏林战役是第二次世界大战欧洲战场的最后一次大规模战斗，同时也是苏德战争期间苏联和德国进行的最后一场大规模战役。1945年，同盟国和苏俄已经相继从不同方向攻入的德国本土。此时，对于德国来说，他的纳粹政权的覆灭只是一个时间问题。对于苏联来说，占领柏林可以获得至高无上的荣誉，毕竟柏林也是法西斯德国大本营以及纳粹最大的巢穴。谁要是能占领了柏林，谁在。二次世界大战结束之后，可以获得至高无上的一个地位。所以这一次苏联的从上到下，从高层到基层，大家。突奇团结一致，然后以柏林为目标进行了一次不惜代价的强攻。
 发言人 1  00:01:15
 此时苏军已经进抵到奥德河、尼斯河一线，也就是今天德国和波兰的边境地区，距离柏林只有60公里。同时，英美联军才刚刚到达易北河一带，距离柏林还有一百到一百二十公里。显而易见，从其当前部署的位置来看的话，苏联已经获得了先发制人的一次机会。此时对于纳粹德国来说可以说是丧钟敲响的开始此次行动由。
@@ -13046,70 +10397,9 @@
 好，那咱们时间差不多了，咱可以。
 发言人 1  00:16:03
 OK下一个下一个章节，大家准备一下。</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>专题讲座</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t># 柏林战役史实研讨：背景、进程与战后格局
-## 讲座概况
-本次研讨会以柏林战役为主题，主讲人系统梳理了战役背景、双方兵力部署、战役进程、希特勒自杀细节、苏军占领柏林及德国投降等史实，并围绕城市作战特点、英美未攻柏林原因、影视推荐、战役持续时间及战后格局等问题与听众展开互动。会议指出，柏林战役是二战欧洲战场的最后一次大规模战斗，也是苏德战争期间苏联与德国进行的最后一场大规模战役。1945年，同盟国与苏俄已从不同方向攻入德国本土，纳粹政权覆灭只是时间问题。对苏联而言，占领柏林可获至高无上的荣誉与战后地位，因此苏军从上到下团结一致，以柏林为目标展开不惜代价的强攻。战役自1945年4月16日持续至5月2日，苏军以约250万兵力对德军约100万守军形成合围，最终攻克柏林，5月9日德国无条件投降，二战欧洲部分正式结束，战后德国分裂为东西两个德国，奠定了冷战欧洲部分的基调。
-## 核心观点
-### 战役背景与双方部署
-- **苏军占据先发优势**：苏军进抵奥德河、尼斯河一线，即今德国与波兰边境地区，距柏林仅60公里；英美联军刚到达易北河一带，距柏林100至120公里，苏联已获先发制人机会。
-- **苏军兵力部署**：苏军由白俄罗斯第一方面军（指挥官朱可夫元帅）与乌克兰第一方面军（指挥官科涅夫元帅）组成，前者从奥德河法兰克福方向北部对柏林突击包围，后者由克拉科夫及德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。
-- **德军防守力量**：主要为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵（民兵，由老人与16岁以下孩子组成），总计约100万人。
-- **苏军兵力规模**：两个方面军总计约250万人，从北部什切青到南部德累斯顿形成合围网。
-### 战役进程与关键节点
-- **第一阶段（4月16日起）**：苏军以数以千计的火炮和喀秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击。
-- **进抵城区**：因德军在桑多梅日桥头堡的防线修筑，苏军至4月20日左右才进抵柏林城区（今柏林潘科区及帕卡洛镇一带）。
-- **突入市区**：4月24日由白俄罗斯第一方面军突进柏林市区，乌克兰第一方面军仍在艰难向柏林边缘靠近，德军温克第十二集团军与苏军持续周旋。
-- **战役定性**：主讲人确认，柏林战役是人类历史上最大规模的城市作战。
-### 希特勒自杀与细节争议
-- **自杀经过**：1945年4月30日，柏林已被苏军围死，苏军距希特勒地堡仅两条街，希特勒不甘被俘，与妻子爱娃·布劳恩一同举枪自尽。
-- **尸体处理与争议**：其尸体被部下用汽油焚烧，至今未见全貌，仅剩烧焦残骸，因缺乏确切证据，外界说法不一，谣言流传。
-- **民间说法分歧**：除少数亲信外，大部分人以自欺欺人的方式麻痹自己继续战斗，导致民间说法褒贬不一。
-### 战后结局与影响
-- **战役结束**：4月29日希特勒与爱娃·布劳恩举行婚礼，4月30日双双自杀；4月30日夜间苏军占领德国国会大厦；5月2日柏林德军全部缴械投降，柏林城防司令魏德林宣布投降，柏林战役结束。
-- **残余部队投降**：仅第九集团军及温克第十二集团军残余部队在温克率领下渡过易北河向英美盟军投降。
-- **德国无条件投降**：5月9日德国宣布无条件投降，将所属领空、领海、机械设备及仍控制的海外属地（荷兰、丹麦、挪威、波罗的海三国地区、捷克斯洛伐克）无条件交与英美盟军及苏俄最高统帅，二战欧洲部分正式结束。
-- **战后格局**：德国分裂为东西两个德国，沿罗斯托克至图林根一线分界，直至1990年统一，奠定了冷战欧洲部分的基调。
-## 金句总结
-&gt; “占领柏林可获至高无上的荣誉与战后地位，因此苏军从上到下团结一致，以柏林为目标展开不惜代价的强攻。”
-&gt; —— **主讲人**（讲到苏联强攻柏林的战略动机时）
-&gt; “柏林战役是人类历史上最大规模的城市作战。”
-&gt; —— **主讲人**（界定战役性质时）
-&gt; “美军的统帅艾森豪威尔认为当时如果说是美军去攻占柏林会增加不必要的伤亡，同时你占领了柏林，你还是要只是把西柏林占在自己的手里。”
-&gt; —— **主讲人**（解释英美未攻柏林原因时）
-## Q&amp;A 环节
-**发言人 4**：那为什么就是英美他不打柏林呢？
-**主讲人**：盟国事先已达成协议柏林战后属苏联；艾森豪威尔认为攻占柏林会增加不必要伤亡且得不偿失，不如占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等德国精华地带；且盟军还需苏联对日作战。
-**发言人 3**：城市作战有什么特点？
-**主讲人**：城市作战中敌军可从建筑或街道各处发动攻击，坦克和车辆在街道上易遭火箭筒和机枪袭击，作战困难且危险。
-**发言人 5**：有什么相关影视作品可以推荐？
-**主讲人**：推荐苏联拍摄的《柏林战役》与德国拍摄的《帝国的毁灭》，前者强调从高层到基层的描写，后者侧重希特勒最后生平及人事任命。
-**发言人 5**：有什么相关书籍可以推荐？
-**主讲人**：建议阅读朱可夫自传、崔可夫自传及斯大林传记中关于柏林战役后苏俄与西方博弈的内容。
-**听众补充**：易北河会师为偶然事件；红旗插上国会大厦照片为临时用床单和颜料绘制并摆拍。</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>4609/2191</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="13.5" customHeight="1" s="9">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:02
+  </si>
+  <si>
+    <t>发言人 1  00:00:02
 嗯，你买房不是生活中哪些约定俗成的规则其实很不合理，比如必须结婚。
 发言人 2  00:00:13
 必须买房，还有必须结婚生子。
@@ -13241,60 +10531,9 @@
 够了，行。
 发言人 2  00:10:56
 ok停吧，ok，哎，停。</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议为多人参与的开放式闲聊讨论，围绕生活中约定俗成规则（如必须结婚、买房、工作）的合理性展开，进而延伸至理想工作形态、AI与机器人的角色分工、机器人拥有思想意识后的潜在风险等话题，最后转向语音分离标注的技术细节。整体氛围轻松随意，未形成明确决策或共识。关于生活规则，发言人1认为买房、结婚等规则在经济不好时并不可行，发言人2指出结婚、买房、升职均取决于个人能力和经济条件，发言人3则认为人必须工作是合理的。在理想工作形态方面，发言人1提出每天按兴趣干活是理想状态，发言人4提出不干活更好的可能性，发言人3举例宠物博主每天发宠物视频即可赚钱，发言人2补充游戏高手也是好工作。针对脏活累活无人承担的问题，发言人3主张应让AI承担苦活累活，而非从事创作艺术类工作。关于机器人思想意识与风险，发言人2引用《终结者》剧情，担心机器人有思想后反抗人类，发言人3提及斯皮尔伯格《人工智能》电影的结局，发言人5认为机器人只需执行命令、不需要思想，发言人3则认为智能和思想可能无法分开。讨论还涉及扫地机器人、做饭机器人、排雷机械狗、单兵外骨骼等应用，以及《重返德军总部》超级战士和数码宝贝中的机器人角色。语音分离标注技术讨论中，发言人3提出多人同时说话时需测试，发言人1指出标注的人需要认识声音，并认为单麦克风效果较强。
-## 要点梳理
-### 1. 讨论生活中的不合理规则
-- 发言人1提出买房、结婚等规则不合理，经济不好时更不可行。
-- 发言人2认为结婚、买房、升职都取决于个人能力和经济条件。
-- 发言人3认为人必须工作是合理的。
-### 2. 理想工作形态与AI分工
-- 发言人1认为理想工作是每天按兴趣干活。
-- 发言人4提出不干活更好的可能性。
-- 发言人3举例宠物博主工作好，每天发宠物视频赚钱。
-- 发言人2提到游戏高手也是好工作。
-- 发言人3主张让AI做苦活累活，而不是创作。
-### 3. 机器人思想意识与风险
-- 发言人2引用《终结者》剧情，担心机器人有思想后反抗人类。
-- 发言人3提到斯皮尔伯格《人工智能》电影的结局。
-- 发言人5认为机器人只需执行命令，不需要思想。
-- 发言人3认为智能和思想可能无法分开。
-### 4. 机器人应用与军事科技
-- 发言人5提到扫地机器人，未来可能有做饭机器人。
-- 发言人2提到军队使用单兵装甲外骨骼、智能枪械等。
-- 发言人3确认排雷机械狗和单兵外骨骼已在应用。
-- 发言人2引用《重返德军总部》超级战士和数码宝贝中的机器人角色。
-### 5. 语音分离标注技术讨论
-- 发言人3提到语音分离，多人同时说话时需测试。
-- 发言人1指出标注的人需要认识声音。
-- 发言人1认为单麦克风效果强。
-## 结论与决定
-本次会议为开放式闲聊讨论，未形成明确决策或共识。</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>3931/1186</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="13.5" customHeight="1" s="9">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 我问呢，我感觉刚才才是才是会议的这个场景。对，开始了，接着争论吧，接着争论吧。我怎么记得啊，开始了。对，开始。
 发言人 1  00:00:10
 哥斯拉这个电影呢，大家耳熟能详，在上个世纪的1954年的时候，就第一部哥斯拉题材的电影就诞生了。迄今为止已经差不多70多年了，然后不管是日本还是美国，翻拍出了不同版本的哥斯拉。但是最早的一个哥斯拉的起源就是在海底的一个生物，由于吸食了核废料、核废水之后啊，然后变变异成了一个庞然大物，然后对人类世界展开一次报复和攻击。然后。
@@ -13372,52 +10611,9 @@
 当时前几年好像还还有个电视剧还是看。好像有电影都跟音乐，这个游戏好像也有类似于这种，使命召唤4，然后那一关，在那个就是反派，当时就是车臣派。军要去那个切尔诺贝利去那个挖核废料的时候，被那个英国 SAS 特种部队那个主角，然后狙杀，结果没狙杀成功，打断一条胳膊，就是那个双狙人那一关。
 发言人 2  00:15:17
 这一条差不多了。大家可以关一下啊。</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议为非正式闲聊式讨论，由两位发言人围绕哥斯拉系列电影展开，并延伸至核废水排放、切尔诺贝利核事故等现实话题。会议无明确议程，未形成正式决议，整体氛围轻松随意。发言人1系统梳理了哥斯拉系列电影的发展脉络：首部电影诞生于1954年，哥斯拉的起源设定为海底生物吸食核废料后变异为庞然大物，在日本神话中是大自然的守护神。美版剧情方面，2014年《哥斯拉》中哥斯拉与人类携手消灭以核废料为能源的雾托物种；《哥斯拉怪兽之王》中反派基多拉为外星生物；《哥斯拉大战金刚》中人类反派将基多拉残骸加装机械装甲制成机械基多拉。日版剧情方面，2016年《新哥斯拉》中哥斯拉最终以无人机投放炸弹耗尽能量，并以冷冻剂封印。讨论还涉及哥斯拉与奥特曼的关联，以及日本核废水排放、切尔诺贝利核事故封存措施等现实话题。
-## 要点梳理
-### 1. 哥斯拉电影系列剧情讨论
-- **系列起源**：哥斯拉首部电影诞生于1954年，距今约70余年，美日两国多次翻拍。
-- **角色设定**：哥斯拉起源为海底生物吸食核废料/核废水后变异成庞然大物，在日本神话中是大自然的守护神，因人类频繁核试验破坏生态而向人类报复。
- - 2014年美国版《哥斯拉》中，哥斯拉与人类携手消灭了以核废料为能源的雾托物种。
- - 《哥斯拉怪兽之王》中反派基多拉为外星生物，人类试图用核武器对付基多拉未果，反致哥斯拉险被溺死，后人类以核废料唤醒哥斯拉击败基多拉。
- - 《哥斯拉大战金刚》中人类反派将基多拉残骸加装机械装甲制成机械基多拉，最终金刚与哥斯拉联手将其击败。
-- **日版剧情**：2016年日本版《新哥斯拉》中，哥斯拉吸收核废料不断升级，人类武器攻击反而增强其战斗力，最终以无人机投放炸弹耗尽能量，并以冷冻剂封印。
-- **立场分歧**：发言人1认为哥斯拉是正面形象，作为大自然守护神，在基多拉降临地球时与人类携手对抗；发言人2反驳称哥斯拉在哥斯拉系列中有时是反派。
-### 2. 哥斯拉与奥特曼等IP的关联讨论
-- **导演关联**：哥斯拉与奥特曼的导演均为圆谷英二，但分属不同时间线。
-- **角色设定差异**：哥斯拉是地球本土物种，奥特曼来自奥特之星，且均为正面形象，难以直接对战。
-- **怪兽联动**：拉顿（翼龙）在奥特曼系列中与奥特曼战斗过。
-### 3. 核废水与核事故现实话题延伸
-- **核废水排放**：日本核废水排放引发对海产品安全的担忧。
-- **个人经历**：发言人2在日本留学期间购买中国进口鱼类，并指出日本国产食品价格昂贵。
-- **切尔诺贝利对比**：切尔诺贝利核事故后，反应堆被水泥封存，普里皮亚季和切尔诺贝利成为鬼城，方圆百里为无人区。发言人1认为日本核废水排放比切尔诺贝利封存措施更不负责任。
-## 结论与决定
-本次会议为非正式闲聊式讨论，未形成正式决议或共识结论。讨论中仅出现一处立场分歧：关于哥斯拉是否为正面形象，发言人1认为哥斯拉作为大自然守护神与人类携手对抗外星生物，发言人2则指出哥斯拉在系列中有时是反派角色。该分歧未达成一致结论。</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>5319/1291</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="13.5" customHeight="1" s="9">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:01
+  </si>
+  <si>
+    <t>发言人 1  00:00:01
 然后咱们这一场大家来分享一下，18岁以前有没有什么特别印呃深刻的印象和记忆？就比如说以前逃课，要么去网吧打游戏，要么去追星，然后还有要么就是去那个是什么呢？去呃谁的哪个音乐会，就是现场或者说有个乐队什么的这一块，然后大家都可以分享一下。
 发言人 2  00:00:27
 我我十八岁之前还真真真没逃过课我上了大学之后啊他有个逃过逃过一次课。
@@ -13641,69 +10837,9 @@
 就是外导。
 发言人 4  00:14:53
 嗯像小会吃的。</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>小组讨论</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t># 青春记忆分享会：逃课、游戏与流行文化回顾
-## 讨论议题
-本次分享会以“18岁以前的深刻印象和记忆”为主题，由主持人发起，六位发言人围绕逃课经历、流行游戏、漫画小说及影视作品等话题展开轻松自由的交流。与会者依次回忆了初中高中的娱乐生活，从走读放学后聚集游戏厅网吧，到高中追星搞乐队，再到对各类单机与网络游戏的深入探讨，整体氛围以个人经历分享和观点交流为主，呈现出对青春时代流行文化的集体怀旧与多元解读。讨论中既有对穿越火线、CS等射击游戏的立场交锋，也有对求生之路剧情设定、游戏与电影先后顺序等话题的深入探究，最终在轻松开放的交流中自然收束，未形成正式决议或行动项。
-## 发言要点
-### 逃课经历与校园生活
-- **发言人 2**：18岁之前没逃过课，大学逃过一次课。
-- **发言人 3**：认为逃课是正常现象。
-- **发言人 4**：补充上大学后就不算逃课了。
-- **发言人 1**：初中走读，每周一下午四点放学，因老师和校领导集中学习座谈，大家常聚集于游戏厅和网吧；当时流行的游戏包括穿越火线（CF）、反恐精英online（CS online）、使命召唤、战地及魔兽等。高中因高考压力不敢逃课，转而追星并组建乐队，涉及架子鼓、电吉他、贝斯，追求朋克金属风格音乐。
-### 流行文化与阅读
-- **发言人 5**：特别喜欢郭敬明的小说。
-- **发言人 2**：提到郭敬明的《梦里花落知多少》，称阅读时感到难受。
-- **发言人 4**：班上流行看名侦探柯南。
-- **发言人 1**：当时流行看柯南和香港漫画老夫子。
-- **发言人 2**：当时看《意林》《读者》《故事会》等杂志。
-### 流行电脑游戏
-- **发言人 4**：小学和初中流行摩尔庄园、赛尔号；认为仙剑三最火且有电视剧。
-- **发言人 1**：初中流行CS online，高中流行求生之路等单机联机游戏；提到劲舞团。
-- **发言人 2**：提到穿越火线、地下城与勇士；解释魔兽争霸是单机、魔兽世界是网游；认为英雄联盟和DOTA有鄙视链，王者荣耀处于最底端。
-- **发言人 5**：玩过仙剑四。
-### 第一人称射击游戏与暴力元素
-- **发言人 4**：提到穿越火线。
-- **发言人 1**：因在贴吧和QQ空间写文章骂穿越火线而被平台封禁，转而成为CS铁杆粉丝，并提到喜欢CS的僵尸模式；解释求生之路第二部因血腥暴力有年龄限制，未成年人不能注册Steam账号（需18岁以上）；求生之路中主角团为无症状感染者，被正常人攻击，病毒类似狂犬病狂暴病毒；制作团队精准预测了美国政府在面对大灾难时的表现，2020年新冠疫情爆发后游戏重新火爆。
-- **发言人 5**：质疑当时游戏没有年龄限制，认为求生之路等游戏暴力，小孩不能玩。
-### 游戏与电影关系及后续讨论
-- **发言人 2**：询问游戏和电影的先有顺序；提到植物大战僵尸有变态版，后期满屏子弹导致电脑卡顿。
-- **发言人 1**：解释生化危机先有游戏后有电影；求生之路是在惊变48小时和生化危机基础上先有电影后有的游戏；变形金刚先有玩具，后有MV和电影（绿日乐队）；分析使命召唤黑色行动基于冷战时期美苏真实历史，现代战争虚构，并认为结合当前俄乌冲突，游戏有点高估俄罗斯。
-- **发言人 4**：提问变形金刚的先有顺序。
-- **发言人 3**：玩塔防游戏如植物大战僵尸、Kindle rush。
-## 共识与分歧
-### 达成共识
-- **逃课经历普遍性**：与会者普遍认同逃课是学生时代的常见现象，且上大学后不再视为逃课。
-- **青春流行文化怀旧**：对穿越火线、CS、魔兽、求生之路等游戏，柯南、老夫子等漫画，以及《意林》《读者》等杂志的共同记忆，构成对青春时代流行文化的集体怀旧。
-### 主要分歧
-- **穿越火线与CS之争**：发言人1认为穿越火线抄袭CS，自己因写文章骂穿越火线被封禁，转而成为CS铁杆粉丝；发言人4则提到穿越火线作为流行游戏的印象，双方对两款游戏的评价立场不同。
-- **暴力游戏与年龄限制**：发言人5质疑当时游戏没有年龄限制，认为求生之路等暴力游戏不适合小孩玩；发言人1解释求生之路第二部因血腥暴力有年龄限制，未成年人不能注册Steam账号，认为暴力设定有其合理性。
-## 未决问题
-- **游戏与电影先后顺序的个案差异**：讨论中确认了生化危机先有游戏后有电影、求生之路先有电影后有游戏、变形金刚先有玩具后有MV和电影等个案，但未形成判断游戏与电影先后顺序的通用规律，后续可进一步探讨不同IP的媒介演化路径。
-- **使命召唤系列剧情设定的现实参照**：发言人1分析黑色行动基于冷战时期美苏真实历史、现代战争虚构，并认为结合当前俄乌冲突游戏有点高估俄罗斯，该观点仅代表个人判断，未展开深入论证，后续可进一步探讨游戏剧情与现实政治的映射关系。</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>6453/2034</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="13.5" customHeight="1" s="9">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:02
+  </si>
+  <si>
+    <t>发言人 1  00:00:02
 啊，然后大家讨论一下，待会儿说啥吧。
 发言人 2  00:00:05
 就是不是红楼了继续吧，梦婷，还没说完，他那个。
@@ -13961,82 +11097,9 @@
 等一下那个咱们时间差不多了咱们再起一条好吧好的好大家现在暂停就是。
 发言人 2  00:14:17
 说一下ok那下一个场景是啥你接。</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>小组讨论</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t># 古典小说细节研讨与人物命运交流
-## 讨论议题
-本次会议为一场多人参与的闲聊式读书讨论会，围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说的情节、人物与细节展开。与会者从《红楼梦》的四大家族、官场暗线、冷香丸等细节切入，随后转向《金瓶梅》与《水浒传》的关系、西门庆的结局与官场描写，再对比《西游记》中佛教的虚伪，最后涉及《红楼梦》的朝代背景与作者映射。整体氛围轻松随意，话题跳跃，未形成正式决议。
-## 发言要点
-### 《红楼梦》四大家族与官场暗线
-- **发言人3**：王熙凤前期的地位和后面的地位高，与其兄长在官场上的地位相关；她结局惨是因为兄长先死。
-- **发言人4**：质疑四大家族看似厉害实则人丁稀少，"就说他们是四大家族，但是感觉就没几个人呀，每家都两家人还多一点"。
-- **发言人3**：薛宝钗家主要是做生意的，有钱但没什么靠山。
-- **发言人1**：背诵四大家族护官符诗句——"贾不贾，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁"。
-- **发言人4**：感叹四大家族看似厉害实则走下坡路。
-- **发言人3**：四大家族整体都在走一个下坡路，映射王朝家族的衰败。
-### 《红楼梦》生活细节与薛宝钗结局
-- **发言人4**：小时候看《红楼梦》对吃螃蟹讲究、尼姑庵泡茶讲究等细节印象深刻。
-- **发言人3**：冷香丸需要雨水那日的雨水、小雪那日的雪，且要正好碰上每个节气。
-- **发言人1**：补充冷香丸配方——春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
-- **发言人3**：120回版本中薛宝钗嫁给贾宝玉，但好多人说是无性婚姻，因为贾宝玉不久就出家了；另一个版本中她后来怀了一个孩子。
-- **发言人2**：质疑孩子是否是贾宝玉的。
-- **发言人3**：认为是狗血版本。
-### 《金瓶梅》与《水浒传》的关系及西门庆结局
-- **发言人1**：《金瓶梅》从武松杀武大郎之后开始写，武松有报仇线但未成功，被高官和权势压制。
-- **发言人2**：询问西门庆与宋江等人是否有交集。
-- **发言人3**：认为应该不会写。
-- **发言人2**：询问西门庆在两个版本中的结局。
-- **发言人3**：《金瓶梅》中西门庆从楼上翻下去逃过一劫，后来武松被发配；西门庆的结局是纵欲过度而死。《水浒传》中武松直接砍了西门庆的头。
-- **发言人4**：西门庆与中央（童贯等）攀上线，成为当地一霸。
-### 《金瓶梅》人物与细节讨论
-- **发言人4**：询问潘金莲在《金瓶梅》中的定位。
-- **发言人3**：西门庆有大约十个老婆，潘金莲属于有心机、比较强势的类型；西门庆有一个老婆生病后去看和尚、不去治病，结果死了。
-- **发言人3**：《金瓶梅》中佛教被描写得很黑，收灯油钱。
-### 《西游记》佛教虚伪与《红楼梦》朝代背景
-- **发言人1**：《西游记》中如来佛祖说天庭派人帮国家后收了300两黄金。
-- **发言人2**：补充狮驼岭和寺院住持贪图袈裟引火自焚的例子，体现佛教虚伪。
-- **发言人2**：询问《红楼梦》是否有真实历史事件。
-- **发言人3**：《红楼梦》没有明确朝代，是虚构故事，但作者映射当时时代。
-- **发言人4**：提到作者映射时代和曹雪芹经历的说法。
-- **发言人1**：《红楼梦》当时是禁书，不敢说朝代，"都已经不说朝代已经是禁书了，那说朝代更禁"。
-### 东吴二宫之争类比
-- **发言人2**：将潘金莲的心机类比到东吴二宫之争中的王夫人和孙鲁班，提到她们搅乱东吴政局。
-- **发言人3、发言人4**：表示了解不多。
-## 共识与分歧
-### 达成共识
-- **四大家族整体衰败**：四大家族虽在护官符上形容得很厉害，但整体都在走下坡路，映射王朝家族的衰败。
-- **《金瓶梅》与《水浒传》的承接关系**：《金瓶梅》从武松杀武大郎之后开始写，武松报仇线未成功，被高官和权势压制。
-- **《红楼梦》无明确朝代**：《红楼梦》没有明确朝代，是虚构故事，但作者映射当时时代。
-### 主要分歧
-- **四大家族是否人丁稀少**：发言人4认为四大家族感觉就没几个人，每家就两家人还多一点；发言人3解释薛宝钗家主要是经商有钱，但未直接回应人丁问题。
-- **《红楼梦》为何不写明朝代**：发言人3认为《红楼梦》开头写得很虚，没有明确朝代；发言人1认为《红楼梦》当时是禁书，不说朝代已经禁了，说朝代更禁。
-## 未决问题
-- **《金瓶梅》中宰相或丞相的结局**：讨论中提及西门庆与中央（童贯等）攀上线，但宰相或丞相的具体结局未展开，待后续查阅或讨论。
-- **《金瓶梅》中西门庆与宋江等人是否有交集**：发言人3认为应该不会写，但未给出确切依据，待进一步考证。
-- **《红楼梦》中四大家族是否人丁稀少**：发言人4质疑书中四大家族人数不多，发言人3未正面回应，书中实际人物规模待进一步梳理。
-- **《西游记》中如来佛祖收300两黄金的章节**：发言人1提及该情节，但具体章节未确认，待后续查阅。</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>5893/2147</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="13.5" customHeight="1" s="9">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:02
+  </si>
+  <si>
+    <t>发言人 1  00:00:02
 行，那我们就提前聊一聊，嗯，你们小时候也不看小说吗？
 发言人 2  00:00:10
 没有，不怎么看小说，可能刷短剧多一点吧。
@@ -14306,50 +11369,9 @@
 还电量不足了。
 发言人 1  00:13:02
 哎，那这些都没填啊，这几个呢，那个好像。</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议为非正式闲聊式交流，与会人员围绕个人阅读习惯、综艺喜好、专业背景及生活话题展开轻松讨论，并尝试切换至日本现代化转型等深度话题，但因人员调度与设备问题未能深入。会议整体氛围轻松，未形成正式决议或行动项。在个人阅读与综艺喜好环节，发言人1表示《红楼梦》阅读多遍，高中初读时理解有限，反复阅读后才发现趣味；发言人2表示不常看小说，偏好短剧，与发言人4均以娱乐综艺为主要观看内容。发言人1提及《种地吧》综艺，介绍其由十位偶像路线男艺人组成，录制周期约半年，近乎24小时连续录制，并成立农业公司尝试新型农业创业，种植小月季与水培蔬菜，项目有亏有盈。在专业背景环节，发言人2为俄语专业但未从事相关职业，发言人1本科数学后转学统计，发言人4为软件工程专业。会议后期发言人5与发言人6加入，提议讨论日本现代化转型与和平宪法，因人员调度及设备电量不足中断，讨论未深入展开。
-## 要点梳理
-### 1. 个人阅读与综艺喜好讨论
-- **阅读习惯**：发言人1表示《红楼梦》看了很多遍，高中时作为推荐读物初读，反复阅读后才发现有趣；发言人2表示不怎么看小说，刷短剧较多。
-- **综艺偏好**：发言人2和4表示看电视剧和综艺较多，偏好娱乐综艺，烧脑内容读不下去，认为工作已耗费脑力，休息时倾向轻松内容。
-- **《种地吧》综艺介绍**：发言人1提及该综艺，十个男孩子组成组合，录制周期约半年，近乎24小时连续录制。
- - 参与者成立农业公司，种植小月季和水培蔬菜，项目有亏有盈。
- - 参与者为实际股东需自担盈亏，但个人主要收入仍来自综艺本身。
- - 发言人4询问录制周期与种植内容，发言人1补充农业门槛较高，如种植月季需聘请专业人员管理水土。
-- **其他节目**：发言人1提及英国综艺《克拉克森的农场》。
-### 2. 专业背景与个人话题
-- **专业背景**：发言人2为俄语专业，就业未从事俄语相关工作，5-6年未用已遗忘，并提及俄罗斯贸易信息多内部消化、对外营销较少；发言人1本科数学，后学统计；发言人4学软件工程，属于工科。
-- **洗发水使用心得**：发言人4表示洗发水换着用，目前囤有三种，头发不易油，并承诺稍后查找订单告知具体品牌。
-### 3. 话题切换与会议收尾
-- **话题提议**：发言人6提议讨论日本现代化转型与和平宪法，发言人5表示对此话题不熟悉，发言人6建议改谈日本现代化之路。
-- **会议中断**：因人员调度及设备电量不足等问题，讨论未深入展开，会议结束。
-## 结论与决定
-本次会议为非正式闲聊式交流，未形成正式决议或行动项。后续可另行安排时间，就日本现代化转型与和平宪法话题进行深入讨论，需提前准备相关资料；发言人4承诺查找并告知所使用洗发水的具体品牌，通过订单记录确认后分享给发言人2。</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>5310/1183</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="13.5" customHeight="1" s="9">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 北部的高丽以及南部的百地与新罗，从分裂到统一的一个整合，然后再到二次世界大战结束之后的一次再次分裂的一个状态。1945年第二次世界大战结束之后，尤其是在亚洲这边，日本投降之后，美国和苏联的军队单独开进了朝鲜北。北部和南部的不同地域，双方以北纬38度为基准，形成了后来广为人知的三八线这一带。尤其在一九四九年，当新中国建立之后，然后我们这边宣布要废除列强在华的一切租界以及特权之后，其中也包含了苏联的利益在里边，尤其是苏联当时在东北建立的中长铁路以及。大连旅顺就是特区的一个存在，然后要中国这边要收回苏联在这一地区的主权。然后当时苏联比较不甘心吧，然后他鼓动当时就是朝鲜去进攻韩国，希望朝鲜能把韩国统一之后能以朝鲜半岛的。相同的，以仁川或者釜山这一块类似的城市来代替，就是旅顺和大连的这样一个地位。然后苏联还要继续在亚洲发挥它该有的一个影响力。
 发言人 1  00:01:37
 就这样，在一九五零年六月的时候，呃，由北朝鲜军队率先越过三八线向南进攻之后，然后朝鲜战争爆发，然后各方有不同的称谓在这场战争中。朝鲜方面称为祖国统一解放战争然后中国这边称为抗美援朝韩国称。为625事件，然后美国以及西方国家称之为朝鲜战争，或者说是韩战。这主要是台湾地区的一个称谓，在战争开始的时候，朝鲜人民军从三八线一直打到了洛东江环形防御圈，差不多也就是今天大邱到釜山一带，就是韩国的这个城市地区。然后后来是美国下场，并于1950年9月15号的时候在仁川。登陆成功之后，将深入到韩国境内的朝鲜人民军分割包围，逐次歼灭，然后以此来收复整个三八线以南的韩国领土。
@@ -14489,73 +11511,9 @@
 但是由于美国后期又越过三八线，向朝鲜以及中朝边境进发，然后触动了咱们的一个敏感神经，唇亡齿寒这么一个概念，就是深入人心。所以说导致了就是即便不愿意和美国爆发全面战争，但是又不得不进行一个全面战争，因为台湾那个事儿已经让咱们已经很被动了，朝鲜半岛这一场，既然。要就是争取战略。主动，那就索性就是解放军的陆军当时就很强，就是在陆地上进行战斗。既然海上没办法进行战斗，那就只能在陆地上进行战斗。所以说这也是后来咱们当时就是一种战斗意志的体现，就是在长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。就这样。
 发言人 2  00:24:27
 OK好，那咱们差不多大家可以关一下，这个录的比较久，已经25min。</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>专题讲座</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t># 朝鲜战争历史脉络与影响研讨会纪要
-## 讲座概况
-本次研讨会以朝鲜战争为主题，主讲人系统梳理了朝鲜半岛从分裂到统一再到二战后再次分裂的历史脉络，深入讲解了战争的爆发背景、主要战役进程、停战协定及战后影响，并围绕战争意义、朝韩现状、朝鲜旅游、军队战斗力、中美关系等议题与与会者展开自由问答。主讲人指出，1945年二战结束后美苏军队分别进驻半岛南北，以北纬38度为界形成三八线；1949年新中国废除列强在华特权，苏联为保留在亚洲的影响力鼓动朝鲜进攻韩国，导致1950年6月朝鲜战争爆发。战争历经多次战役，最终于1953年7月27日签署停战协定，朝韩名义上停战但未实现真正和平。主讲人从中国、美国、朝韩三方角度剖析战争影响，强调朝鲜战争奠定中国强国地位，美国首次在未取胜情况下签署停战协定，朝韩同源却分裂至今。讲座以主讲人讲解与自由问答相结合的形式展开，为理解东北亚地缘格局提供了历史纵深。
-## 核心观点
-### 朝鲜半岛分裂源于美苏冷战布局
-- **分裂起点**：1945年二战结束，美苏军队分别进驻朝鲜半岛南北，以北纬38度为界形成三八线。
-- **冷战博弈**：美苏在朝鲜半岛建立缓冲区，美国保护日本免遭共产主义影响，苏联建立卫星国；最初计划类似奥地利普选建立统一政府，但美苏关系恶化，扶植领导人各有心思，最终分裂为两个国家。
-- **战争导火索**：1949年新中国宣布废除列强在华特权，包括苏联在东北的中长铁路及大连旅顺特权，苏联为保留在亚洲影响力，鼓动朝鲜进攻韩国，1950年6月北朝鲜军队越过三八线南攻，朝鲜战争爆发。
-- **各方称谓**：朝鲜称祖国统一解放战争，中国称抗美援朝，韩国称625事件，美国称朝鲜战争或韩战。
-### 战争进程与主要战役
-- **初期战局**：朝鲜人民军初期推进至洛东江环形防御圈（大邱至釜山一带）。
-- **仁川登陆扭转战局**：1950年9月15日美军仁川登陆，分割包围朝鲜人民军；联合国军由16国共同组成，麦克阿瑟任总司令，越过三八线。
-- **中国出兵**：1950年10月19日志愿军跨过鸭绿江，10月25日与韩军首次交火，11月5日第一次战役结束。
-- **后续战役**：第二次战役含长津湖战役；第三次战役越过三八线占领汉城（今首尔），推进至三七线；第五次战役为最后一次大规模战役，双方在三八线附近互有攻防。
-- **停战协定**：1953年7月27日双方签署停战协定，朝韩名义上停战，未实现真正和平。
-### 战争影响与历史意义
-- **中国**：朝鲜战争奠定中国强国地位；1967年越南战争时中国警告美国不得越过北纬十七度线，美国未敢越线。
-- **美国**：称朝鲜战争为"被遗忘的战争"，最后一任司令官马克·克拉克承认是首位在未取胜情况下签署停战协定的司令官。
-- **朝韩**：同源却分裂为两个国家，三八线悲剧延续至今。
-### 朝韩现状与旅游对比
-- **朝鲜旅游限制**：限制人身自由，入境检查手机，无无线网，网络类似中国八九十年代状态，国际漫游和网络昂贵；普通人无法上网，局域网有限，用不起5G手机。
-- **旅游内容**：主要参观平壤主体思想建设成就，类似中国文革时期思想宣传；景点包括平壤志愿军功绩展览、开城（朝鲜半岛三千年古都）特产人参。
-- **韩国对比**：通过韩剧进行意识形态宣传，导致朝鲜脱北者众多。
-### 朝韩统一展望
-- **统一形态**：若朝韩统一，大概率韩国兼并朝鲜，因经济实力和综合国力占优，但北方有优质兵源和核武器，统一将成东北亚不稳定因素。
-- **历史类比**：越南统一后进攻柬埔寨和泰国，中国1979年发动自卫反击战，朝鲜半岛统一后局势更不可控。
-- **苏联角色**：朝鲜战争时苏联提供空军掩护和武器后勤支持。
-### 中俄朝关系与韩军战斗力
-- **中俄朝关系**：各怀鬼胎，图们江出海口问题至今未解决，俄朝建桥封死航道。
-- **韩军战斗力演变**：初期战斗力弱，1950年6月25日战争爆发后，7月10日起南部地面战斗主要由美军和朝鲜人民军进行；1952年后美国整军训练，韩军形成基本战斗力。
-- **韩军文化**：军官主体为二战时期日本人扶植的伪军骨干，士兵类似抓壮丁形式，军队霸凌事件延续至今，充满昭和军国主义思想余孽。
-- **第五次战役表现**：志愿军从韩军战线突破，导致韩军前线崩溃，美军撤销韩国第三军团。
-### 抗美援朝决策与台湾问题
-- **海军实力不足**：台湾与大陆距离约100公里，当时解放军无海军实力，无法渡海作战。
-- **美国亚太布局**：1950年美国参众两院视朝鲜战争为共产主义对自由世界的全面进攻，将台湾和韩国纳入亚太保护圈；美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，防止解放军解放台湾和国民党反攻大陆。
-- **参战动因**：美军越过三八线触动中国敏感神经，唇亡齿寒概念深入人心，中国被迫参战；长津湖和上甘岭战役让美军惨败，成为美国人挥之不去的梦魇。
-## 金句总结
-&gt; "如果当时朝鲜战争爆发的时候，美国没有下场去救援韩国，今日朝鲜可能会是一个苏联的卫星国附属之下的……朝韩要是统一，大概率应该是韩国兼并朝鲜。"
-&gt; —— **主讲人**（讨论朝韩统一展望时，分析美国未下场与统一主导权的假设情形）
-## Q&amp;A 环节
-本次讲座以主讲人讲解与自由问答相结合的形式展开，现场互动问答按主题分组呈现如下。
-**发言人 7**：如果不妨畅想一下，如果当时没有形成这种冷战布局，就是互相争夺这个半岛的控制权的话，这个大一统的朝鲜半岛会是一个什么形态？会是一个大号的朝鲜，还是一个平衡的韩朝？
-**主讲人**：如果美国未下场救援，今日朝鲜可能成为苏联卫星国，威胁美日；朝韩若统一，大概率韩国兼并朝鲜，因经济实力和综合国力占优，但北方有优质兵源和核武器，统一将成东北亚不稳定因素。类比越南统一后进攻柬埔寨和泰国，中国1979年发动自卫反击战，朝鲜半岛统一后局势更不可控。</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>7464/2478</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="13.5" customHeight="1" s="9">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:03
+  </si>
+  <si>
+    <t>发言人 1  00:00:03
 还有一个问题是出门必带的三样东西是什么？
 发言人 2  00:00:08
 手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。
@@ -14727,61 +11685,9 @@
 那个妹子好像没买大雨，她一大早就早上可能就送给孩子，然后就去。
 发言人 4  00:10:13
 好，这一条时间差不多了，我们先停吧。</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>对话记录</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t># 闲聊讨论日常出门必带物品及生活习惯
-## 对话概况
-本次对话为多人参与的闲聊式讨论，围绕“出门必带三样东西”展开，随后自然延伸到头发绑扎、胡子打理、上班携带物品、天气与下雨等生活话题。发言人以个人习惯和经历分享为主，气氛轻松随意，未涉及业务或决策内容。核心对照集中在个人出门物品选择上：发言人2主张手机、充电宝、指甲刀三件套，并强调指甲刀的多功能用途；发言人3补充钥匙为必带物品，而发言人1因使用指纹锁无需带钥匙。话题随后转向形象打理，发言人4必带皮圈绑发，发言人2与发言人1均认为散头发更好看，形成轻微观点差异。整体对话以生活经验交流为主线，各发言人立场如实呈现，未产生正式决议。
-## 交流内容
-### 出门必带物品讨论
-- **发言人1**：提出“出门必带的三样东西”问题，并提到自家门为指纹锁，无需带钥匙。
-- **发言人2**：表示出门必带手机、充电宝、指甲刀，指甲刀可用于刮指甲、磨手掌等；已使用电子锁多年，没有钥匙概念，用指甲刀平替钥匙，以前钥匙上还挂扣耳勺。
-- **发言人3**：补充钥匙为必带物品。
-### 头发绑扎与个人形象讨论
-- **发言人4**：表示出门必带皮圈用于绑头发。
-- **发言人2**：从男性视角好奇女生为何绑发，假设自己是女生会选择披发，认为“要一绑的话，我自个的角度就觉得显得自己脑袋很大”。
-- **发言人1**：认为“绑的没有那个散头发好看，那我自己不想让女生绑”。
-- **发言人3**：补充“弄个公分两边都补点点小点”的发型建议。
-### 胡子打理与个人经历
-- **发言人2**：分享高中时想留长发大胡子的梦想，尝试后因不好打理放弃；留胡子时曾被误认为新疆少数民族；胡子一天能长几毫米，上班必带刮胡刀；上班必带三件套为充电宝、手机、刮胡刀。
-### 上班携带物品与工卡讨论
-- **发言人5**：每天上班带手机、耳机和工卡。
-- **发言人2**：将耳机和工卡放在单位，刷脸进门；认为工卡挂脖在政府系统或外企CBD有必要，平时没必要。
-- **发言人1**：提到领夜宵需带工卡。
-### 天气与下雨讨论
-- **发言人3**：提到每年下雨园区门口都是水，李博家因地势被淹。
-- **发言人2**：建议住三楼以上以防水淹。
-- **发言人4**：认为北京夏天容易下雨。
-## 共识与分歧
-### 达成共识与倾向
-- **散头发更好看**：发言人2与发言人1均认为披发或散头发优于绑发，发言人2认为绑发显脑袋大，发言人1认为散头发更好看。
-### 存有分歧与差异
-- **是否绑发**：发言人4必带皮圈绑头发，而发言人2与发言人1倾向散头发，认为绑发不好看，双方立场不同但均基于个人审美偏好。
-## 延伸话题
-- **工卡使用场景**：发言人2认为工卡挂脖在政府系统或外企CBD有必要，平时没必要，发言人1补充领夜宵需带工卡。
-- **防水淹建议**：发言人2建议住三楼以上以防水淹，源于发言人3提到的李博家因地势被淹经历。</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>3851/1259</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="13.5" customHeight="1" s="9">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:03
+  </si>
+  <si>
+    <t>发言人 1  00:00:03
 咱们刚才那个就先说这个手机里最常用的三个A P P.
 发言人 2  00:00:08
 知乎小红书，然后还有那个就是谷歌。
@@ -14961,64 +11867,9 @@
 但是他的确全球的影响力。
 发言人 2  00:10:13
 其实都对，然后那个就是亚洲，十分钟了，十分钟了，挺好的。</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>小组讨论</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t># 手机常用APP与音乐偏好闲聊讨论
-## 讨论议题
-本次会议为多人参与的闲聊式讨论，围绕手机中最常用的APP、视频播放器、音乐APP及音乐偏好等话题展开，并重点探讨了Taylor Swift重新走红的原因。会议氛围轻松，以个人经验分享为主，穿插中英文混杂表达，未形成正式决议。在常用APP分享环节，发言人2最常用知乎、小红书和谷歌；发言人3最常用微信、抖音、淘宝和京东；发言人4最常用微信、小红书和小布小布（AI助手）。针对AI助手与浏览器的使用，发言人3认为AI小助手更全面、回答更精准、总结性更强，而发言人2对AI的准确性存疑，自嘲仍停留在浏览器加纸质地图、尺子、圆规、铅笔标注的思维模式。在视频与播放器APP讨论中，发言人5常用B站，发言人2常用YouTube，但发言人4指出YouTube手机翻墙困难，发言人5补充单框架手机连YouTube都难以安装。发言人1发现国内付费电视剧在YouTube上免费，发言人2认为大平台有版权纠纷需付费，小网站反而免费。播放器APP方面，发言人3提到腾讯视频、爱奇艺、优酷、芒果TV等，发言人2抱怨广告时间长，倾向用B站直接观看。在音乐APP与听歌习惯环节，发言人5常用网易云音乐，发言人2以前用酷狗、酷我，并提及欧美音乐平台Spotify（虾扎），认为其演唱会版本比国内网易云更多。听音乐时间方面，发言人1在上班时听，发言人4在通勤路上听，发言人2提到在柏林坐地铁听音乐代入感强，并强调要听清音乐内容。在乐队歌手偏好与Taylor Swift走红讨论中，发言人3最近喜欢谢霆锋，提到其演Taylor Swift；发言人1认为五月天以前好，但新发作品唱不上去了。发言人2好奇Taylor Swift为何重新火起来，回忆其在2010年代初期走红，因绯闻消沉后重新火起来，对九零后和零零后都有影响，并提及与猫头鹰之城主唱亚当杨的绯闻。发言人3认为Taylor Swift演唱有感染力、氛围好。
-## 发言要点
-### 常用APP分享
-- **发言人2**：最常用APP为知乎、小红书和谷歌。对AI软件准确性存疑，不确定AI软件说的是否正确，自嘲停留在浏览器加纸质地图、尺子、圆规、铅笔标注的思维模式。
-- **发言人3**：最常用APP为微信、抖音、淘宝、京东。认为AI小助手更全面、回答更精准、总结性比较强。
-- **发言人4**：最常用APP为微信、小红书和小布小布（AI助手）。
-### 视频与播放器APP讨论
-- **发言人5**：常用B站。
-- **发言人2**：常用YouTube，认为大平台有版权纠纷需付费，小网站反而免费。
-- **发言人4**：指出YouTube手机翻墙困难。
-- **发言人5**：补充单框架手机连YouTube都难以安装。
-- **发言人1**：发现国内付费电视剧在YouTube上免费。
-- **发言人3**：提到腾讯视频、爱奇艺、优酷、芒果TV等播放器APP。
-- **发言人2**：抱怨广告时间长，倾向用B站直接观看。
-### 音乐APP与听歌习惯
-- **发言人5**：网易云用得较多。
-- **发言人2**：以前用酷狗、酷我，提及欧美音乐平台Spotify（虾扎），认为其演唱会版本比国内网易云更多；提到在柏林坐地铁听音乐代入感强，强调听音乐要听清内容。
-- **发言人1**：上班时听音乐。
-- **发言人4**：通勤路上听音乐。
-### 乐队歌手偏好与Taylor Swift走红讨论
-- **发言人3**：最近喜欢谢霆锋，提到其演Taylor Swift；认为Taylor Swift演唱有感染力、氛围好。
-- **发言人1**：认为五月天以前好，但新发作品唱不上去了。
-- **发言人2**：回忆Taylor Swift在2010年代初期走红，因绯闻消沉后重新火起来，对九零后和零零后都有影响，提及与猫头鹰之城主唱亚当杨的绯闻；对Taylor Swift重新火起来的原因表示疑惑。
-## 共识与分歧
-### 达成共识
-- **AI助手优势**：发言人3认为AI小助手更全面、回答更精准、总结性更强。
-- **大平台版权付费模式**：大平台有版权纠纷需付费，小网站反而免费。
-- **Taylor Swift影响力**：其演唱有感染力、氛围好，对九零后和零零后都有影响。
-### 主要分歧
-- **AI助手与浏览器之争**：发言人3认为AI小助手更全面、回答更精准、总结性更强；发言人2对AI准确性存疑，倾向传统浏览器加纸质地图的思维模式。
-## 未决问题
-- **Taylor Swift重新走红原因**：发言人2对其重新火起来的原因表示疑惑，未得到明确解答；发言人3认为与其演唱感染力和氛围有关，发言人2回忆其因绯闻消沉后重新走红，但具体驱动因素尚未形成一致结论。</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>4259/1999</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="13.5" customHeight="1" s="9">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 这一章啊，咱们就具体讲一下2022年以来俄罗斯进攻乌克兰之后，俄军在战场上所进行的表现。众所周知，不管是在美国还是在我们国家，还是在西欧国家的认知里面，从苏联时期开始，俄军就一直是给人一种钢铁洪流的一种印象。然后在各国的很多游戏里面，不管是苏联还是俄罗斯，一直是作为电影和游戏中的一种反派的呃那个角色诞生于此。然后呢，呃呃古代也有一种说法，就把俄军称为什么灰色牲口？就是啥呢？它是耗材，因为就是俄罗斯比很多欧洲国家更承受得了更多的、更惨烈的伤亡和那种就是死亡人数，反而所以。这一系列的这种代价是西方国家所不能承受的。
 发言人 1  00:01:04
 可是呢，当2022年俄乌战争爆发的时候，俄军刚进攻乌克兰的时候，全世界都会认为战争天平会向俄罗斯一边倒，然后基辅会很快占领。呃，乌克兰会被消灭，泽连斯基会流亡。可是剧情超出各位的反转和认知，泽连斯基不但扛住了俄罗斯的进攻，反而还把俄军从基辅打回了白俄罗斯和乌克兰的边境。所以说今天。就想和大家探讨一下，关于俄罗斯在俄乌战争的表现是否是俄军它真正应有的一种状态，然后大家发表一下看法，谢谢。
@@ -15178,61 +12029,9 @@
 嗯，明白了。 OK 那咱们录的时间差不多了，咱先停一下，然后让你们。行。
 发言人 1  00:17:22
 好，好。</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>专题讲座</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t># 俄乌战争俄军表现研讨与俄罗斯认知交流
-## 讲座概况
-本次研讨会围绕2022年俄乌战争以来俄军在战场上的实际表现展开，由主持人发起议题，与会者对比了游戏与影视中塑造的俄军形象与现实战场表现，深入分析俄军后勤、指挥、单兵素质等方面的真实状态，并延伸讨论俄罗斯的历史、文化、地缘政治地位以及欧洲对俄罗斯的认知。会议以自由发言和观点交流为主，未形成明确决议。 与会者普遍认为，俄军传统上被视为"钢铁洪流"，但2022年进攻乌克兰时表现与预期严重不符，基辅未被占领，俄军被击退回白俄罗斯和乌克兰边境。分析指出，俄军基层官兵以为行动是演习，进入乌克兰后遭遇民兵自发抵抗，战争从闪电战转为持久战。关于表现不佳的原因，有观点认为普京可能活在自己的信息茧房中，用于策反乌克兰官员的经费被贪污瓜分，导致策反失败；2014年克里米亚事件引发乌克兰民族仇恨，类似九一八事变，激发了乌克兰的抵抗意志。关于俄军战斗力，与会者认为俄军单兵素质强，但后勤和指挥拉垮，被形容为"矮脚巨人"，战场形态落后，类似二战加无人机。会议还讨论了西方游戏对俄军的反派塑造、乌克兰作为"欧洲之门"的地缘意义，以及俄罗斯的历史文化印象。
-## 核心观点
-### 俄军表现与预期严重不符
-- **进攻基辅失败**：2022年俄罗斯进攻乌克兰，俄军初期进攻基辅失败，被击退回白俄罗斯和乌克兰边境，传统"钢铁洪流"形象与现实表现形成强烈反差。
-- **基层认知错位**：俄军基层官兵以为行动是演习，进入乌克兰后遭遇民兵自发抵抗，战争从闪电战转为持久战。
-### 俄军表现不佳的原因
-- **信息茧房与腐败**：普京可能活在自己的信息茧房中；用于策反乌克兰官员的经费被贪污瓜分，导致策反失败。
-- **乌克兰民族情绪**：2014年克里米亚事件引发乌克兰民族仇恨，类似九一八事变，激发了乌克兰的抵抗意志。
-### 俄军战斗力与战场形态
-- **单兵强、整体弱**：俄军单兵素质厉害，但后勤和指挥差，被形容为"矮脚巨人"。
-- **战场形态落后**：俄乌战场与二战相比没有进步，只是多了无人机，双方重装备耗光后转为战壕扔手雷和无人机互炸，俄罗斯无人机依赖伊朗供应。
-- **防守反击型战力**：俄罗斯打仗需要被打到家破国亡才能迸发战斗力，主动进攻表现不佳，防守反击时反而能发挥战力。
-### 游戏与媒体中的俄军形象
-- **西方叙事塑造反派**：游戏如《战地风云》《使命召唤》《红警》中俄军形象与现实中俄军表现有360度反差；红警等游戏由美国制作，旨在抹黑苏联。
-### 俄罗斯地缘政治与欧洲认知
-- **乌克兰的战略地位**：乌克兰被称为"欧洲之门"，欧洲人认为欧亚分界线在乌克兰。
-- **欧洲的排斥逻辑**：俄罗斯被蒙古统治200年，不被欧洲认可，被视为亚洲游牧民族；欧洲支援乌克兰是为了将俄罗斯挡在亚洲之外，防止俄罗斯涉足欧洲。
-### 俄罗斯文化与历史印象
-- **东宫博物馆见闻**：东宫是世界四大艺术博物馆之一，发言人1去了三次未看完藏品。
-- **殖民掠夺的珍宝**：俄罗斯通过殖民掠夺和探险队获得多国珍宝，包括中国西夏王陵、敦煌文物等。
-## 金句总结
-&gt; "反正我感觉俄罗斯打仗就是你得给他打到那个给他打的要不行了，要家破国亡了，他才能迸发出一种战斗力，打防反。"
-&gt; —— **发言人 4**（讨论俄军主动进攻与防守反击的战力差异时）
-&gt; "俄军他总的来说，给我看来，他就是单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上。"
-&gt; —— **发言人 1**（分析俄军战斗力构成时）
-&gt; "感觉俄乌战场打的跟二战时候也没啥进步，多了点无人机，但还是扔手雷的，在这打就是不太先进。"
-&gt; —— **发言人 4**（评价俄乌战场形态时）
-## Q&amp;A 环节
-本次讲座以主旨分享为主，现场未设置问答互动。</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>6103/1603</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="13.5" customHeight="1" s="9">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:01
+  </si>
+  <si>
+    <t>发言人 1  00:00:01
 贝姐啊，咱们主要讲一下那个前段时间那个热播的南京照相馆这部电影。首先还是想问一下大家，关于大家对这场电影的印象是个什么样子的？来吧。
 发言人 3  00:00:18
 我我我看的好像是那个片段，在抖音上看的切片那些。但是切片好像看着还行啊，不知道是什么样。
@@ -15318,61 +12117,9 @@
 你看问的那应该是ok了吧，咱们这一段先结束，然后大家可以暂停那个停止了。
 发言人 1  00:13:48
 13分钟够吧，够10~25min。那下一场我当配角了，大家谁当主角？</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>专题讲座</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t># 《南京照相馆》观影研讨：历史背景与真实细节辨析
-## 讲座概况
-本次研讨会围绕电影《南京照相馆》展开，由主持人引导，与会者首先分享了观影印象。发言人3通过抖音切片了解影片后赴影院观看，评价良好；发言人4将其定位为灾难电影，对地下室多人吃喝睡觉的场景印象最深；发言人2认为影片深刻好看；发言人5因题材沉重未观看。整体观影反馈以正面为主，同时普遍认为题材沉重、观后心情悲痛。 主持人随后系统介绍了南京大屠杀的历史背景。1937年8月13日，国民党军队在上海与日军激战，因实力差距撤退，日军追击至南京。自九一八事变以来，日军占领东北、华北均未遭遇成规模抵抗，八一三淞沪抗战是其首次遭受迎头痛击，战场惨烈、伤亡惨重。日军攻破南京后，因缺乏法律与军纪约束，加之长达四个月的战场应激创伤，最终酿成南京大屠杀。主持人特别指出，原指挥官松井石根因生病被临时替换，其曾发布命令避免烧杀抢掠；接任的朝香宫鸠彦亲王上任后发布第一道命令"不留俘虏，月后祭坟"，直接导致军纪失控，暴行蔓延至平民。 关于电影虚构与真实元素的辨析，主持人澄清电影主要人物均为虚构，但照片拍摄是真实的。与会者还延伸讨论了国内相关纪念馆的参观体验与公众关注度，主持人补充了中华门城墙战斗、挹江门撤退惨案及战后审判等真实历史细节。
-## 核心观点
-### 观影印象以正面为主，题材沉重引发共鸣
-- **整体反馈正面**：发言人3通过抖音切片了解影片，认为片段尚可，赴影院观看后评价"挺好看"；发言人2认为影片"挺深刻、挺好看"。
-- **题材定位沉重**：发言人4将电影定位为灾难电影，印象最深的是地下室多人吃喝睡觉的场景；发言人5因题材不习惯未观看。
-### 南京大屠杀成因：军纪失控与战场创伤叠加
-- **淞沪抗战是转折点**：1937年8月13日，国民党军队在上海与日军激战，因实力原因撤退。自九一八事变、七七事变以来，日军未遭遇成规模抵抗，八一三淞沪抗战是其首次迎头痛击，战场惨烈、伤亡惨重。
-- **军纪约束缺失**：日军攻破南京后，因缺乏法律和军纪约束，加之长达四个月的战场应激创伤，最终酿成南京大屠杀。
-- **指挥官更换是关键变量**：原指挥官松井石根因生病被临时替换，曾发布命令避免烧杀抢掠；接任的朝香宫鸠彦亲王狂热推崇脱亚入欧思想，上任后发布第一道命令"不留俘虏，月后祭坟"，直接导致军纪失控，暴行蔓延至平民。
-### 电影虚构与真实元素：人物虚构，照片拍摄属实
-- **主要人物为虚构**：发言人4质疑主角与日本军官建立友谊的情节是否虚构，主持人澄清电影主要人物均为虚构。
-- **照片拍摄真实存在**：真实历史中，两名美国传教士拍摄了日军暴行；一名负责冲洗照片的中国人偷偷拷贝了日军拍摄的暴行照片，战后递交给国民政府军事法庭作为审判日本战犯的证据。真实历史与电影描述方式不同。
-### 纪念馆参观体验反映公众关注度
-- **多地纪念馆人流量大**：发言人2在沈阳参观伪满洲国博物馆，上午前往下午已排不上队；唐山大地震纪念馆情况类似。发言人3参观上海淞沪会战相关纪念馆，即使下雨人流量依然很大。
-- **南京大屠杀纪念馆预约困难**：发言人4多年前去过，如今预约困难，"抢都抢不到"。
-- **上海宣传较好的原因**：主持人补充说明，中日第一场大规模战斗在上海打响，是自九一八事变以来中国军人第一次真正意义上的抗击。
-### 电影中其他真实历史细节
-- **中华门城墙战斗**：电影开头的中华门城墙战斗是真实历史细节。
-- **挹江门撤退惨案**：撤退时守军未收到撤退命令，宪兵未让平民撤出，信息差导致惨案。
-- **战后审判**：电影尾声审判部分，谷寿夫等主犯被枪决是真实历史。
-- **日本国内否认现象**：发言人5提到现在很多日本人不承认南京大屠杀，主持人对此表示认同。
-## 金句总结
-&gt; "不留俘虏，月后祭坟。"
-&gt; —— **主持人**（介绍朝香宫鸠彦亲王上任后发布的第一道命令，直接导致军纪失控、暴行蔓延至平民）
-&gt; "这个电影里的主要的人物是虚构，但是照片的拍摄是真实的，但不是以电影里所描述的一个方式进行的。"
-&gt; —— **主持人**（回应发言人4关于日本军官角色真实性的质疑，澄清电影虚构与真实元素的边界）
-## Q&amp;A 环节
-**发言人4**：电影中主角与日本军官建立友谊的情节是否虚构？有没有真实原型？
-**主持人**：电影主要人物是虚构的，但照片拍摄是真实的，真实历史与电影描述方式不同。真实历史中，两名美国传教士拍摄了日军暴行，一名负责冲洗照片的中国人偷偷拷贝了日军拍摄的暴行照片，战后递交给国民政府军事法庭作为审判证据。</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>4228/1931</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="13.5" customHeight="1" s="9">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 这一章咱们关于对于日本进行一下探讨啊，首先呢，日本对于咱们中，广大的中国人的印象中，就是一个比较复杂的国家。第一是因为历史原因的时候，对，中英混说，历史原因的时候，就是中日关系确实也发生过战争，然后也发生过一些悲剧。但是另一方面的话，在今天我们国家当时主要的很多外部投资，日本也占。呃，很大的一个比重。然后中日也是主要的一个贸易伙伴吧？所以说这也很复杂。当然今天咱们有很多呃，就是不管是上学的还是上班的，都喜欢去日本旅游。然后日本的服务业和购物体验确实在很多国家之间比起来也是首屈一指。啊，所以说今天咱们谈一谈日本这个国家的一个概况，还有大家对日本的一个印象，还有以及对这个国家的一个了解是什么样的，然后大家都可以自由发言一下，开始吧。/.
 发言人 2  00:01:13
 sil 嗯，我之前还挺喜欢日本，包括我读研的时候我还上了一课，就是去讲日本文化，然后后来我读了一部一部，就。小说就是那个四代同堂，余老舍嗯嗯。
@@ -15444,57 +12191,9 @@
 方法国意大利都是女生买的法国意大利还有就像什么那个韩国买的都很多的对化妆品对男生买就是名牌还有化妆品巧克力然后那个白色链子。对，然后感觉去欧洲他们也是买巧克力，然后去日韩也买巧克力，怎么感觉哪的巧克力都比国内的巧克力好？呃，去日本我最喜欢干的事还是什么呢？去爬，去登山还是，哈哈。就是还是爬山，然后去爬富士山，然后还有去看古城，去逛博物馆，就是这样，去什么镰仓，呃，卡马库拉喽。然后还有那个京都 kod，还有那个就是，呃，对，关西那边是，还有那个丽子雅，就名古屋那边就是有那个独特的那种，就是自己那种，就本土化改良那种，就是文化场景，就古城这样的一个状态。所以说我是比较喜欢那个镰仓那边那种气候，夏天去呢比较舒服。
 发言人 1  00:15:37
 剑科对就建科道口那里在卡玛库拉楼接下来了。是差不多了还有觉可以改成中日。了我我了中日然后是大会场大会场咱们就觉得的。墙边上做的好的。</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>小组讨论</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t># 日本国家概况与文化历史自由研讨
-## 讨论议题
-本次研讨会围绕日本国家概况展开自由讨论，由主持人引导、参与者分享个人见解，氛围轻松，未形成正式决议。讨论涵盖中日历史关系、日本文化来源与三次转型、天皇制度演变、日本旅游与购物体验等话题，以个人经历和知识分享为主，穿插英语交流。主持人开场指出日本是中国主要外部投资来源之一和重要贸易伙伴，同时提及历史战争背景，引导大家分享对日本的印象。讨论整体走向从宏观历史脉络逐步深入到具体文化现象与个人体验，参与者对日本文化的接收与本土化转型逻辑形成较为一致的认知框架，对天皇制度的象征性定位亦有共识，整体倾向以知识分享与观点交流为主。
-## 发言要点
-### 1. 日本印象引入
-- **主持人**：日本在中国对外关系中具有复杂性，既是主要外部投资来源之一，也是重要贸易伙伴，同时存在历史战争背景。日本服务业和购物体验在众多国家中首屈一指。
-### 2. 日本文化来源与三次转型
-- **发言人2**：对日本文化有浓厚兴趣，阅读老舍小说《四世同堂》引发对民族仇恨的思考，并关注日本岛国地理对民族性格的影响。
-- **主持人**：日本文化缺乏原创性，属于外来接收后的本土化转型，经历三次关键转型：
- - 大化改新时期：学习中国吴越文化，形成和服、制茶、漆器等传统。
- - 明治维新时期：学习英国和德国法度。
- - 二战后：美国制定和平宪法，推动社会结构转型。
-### 3. 天皇制度与君主立宪制讨论
-- **主持人**：古代天皇作为吉祥物存在，1945年二战后麦克阿瑟迫使天皇公开露面，打破其神格，推动社会转型。现天皇为象征性存在，无实权，政治由国会和内阁主导。
-- **主持人**：对比英国、西班牙等君主立宪制国家，英国国王因英联邦名义元首身份，影响力大于日本天皇。
-### 4. 日本旅游与购物体验
-- **主持人**：分享个人旅游偏好，喜欢爬富士山、逛古城和博物馆，提及秋叶原、镰仓、京都等地。
-- **主持人**：中古店产业源于广场协议后日本泡沫经济崩溃，催生二手奢侈品寄卖产业，可购得LV、Burberry等上个世纪大牌。
-## 共识与分歧
-### 达成共识
-- **日本文化转型脉络**：日本文化缺乏原创性，经历大化改新、明治维新、二战后和平宪法三次关键转型，各阶段分别吸收中国、英国与德国、美国影响。
-- **天皇制度现状**：天皇为象征性存在，无实权，政治由国会和内阁主导。
-- **中古店产业成因**：广场协议后泡沫经济崩溃催生中古二手店产业。
-### 主要分歧
-本次讨论未出现明显立场分歧，各方观点相互补充，以知识分享为主。
-## 未决问题
-- **日本民众对天皇的崇拜现状**：讨论涉及天皇神格打破与象征性定位，但未深入探讨当前日本民众对天皇的实际态度与崇拜程度，有待进一步调研验证。</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>4892/1190</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="13.5" customHeight="1" s="9">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:01
+  </si>
+  <si>
+    <t>发言人 1  00:00:01
 好，这回咱们再继续刚才那个所谈论的文学啊，咱们聊了西游记了，然后咱们接下来进行一个延伸，然后大家对于三国是一个什么样的一个印象，主要就是。
 发言人 2  00:00:15
 三国。
@@ -15690,74 +12389,9 @@
 大家先停一下吧，下一个话题。那下一个咱们说点什么呢？
 发言人 3  00:19:17
 下一个。咱们可以继续。</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>小组讨论</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t># 三国演义与红楼梦文学内容及历史背景延伸讨论
-## 讨论议题
-本次会议围绕中国古典文学名著展开延伸讨论，先聚焦《三国演义》及其正史背景，涉及赤壁之战、阵营偏好、刘备称王连锁反应、借荆州与湘水划界、白衣渡江、东吴大都督命运、姜维北伐、魏延事件、三顾茅庐与隆中对等话题，随后转向《红楼梦》，讨论其前八十回与后四十回作者差异、判词预示、人物命运解读及版本问题。会议以闲聊式交流为主，发言人多轮互动，最终由主持人提议切换话题结束。
-## 发言要点
-### 三国印象与阵营偏好
-- **发言人2**：三国内容到诸葛亮去世基本完成百分之八九十，看到诸葛亮去世后便不想再看，认为后面没意思；印象最深的章节是赤壁之战。
-- **主持人**：补充正史后续脉络，包括姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降及西晋灭吴。
-- **发言人2**：偏好蜀汉刘备阵营，因其白手起家。
-### 刘备称王与孙刘联盟破裂
-- **主持人**：刘备贸然称汉中王引发连锁反应，导致孙权决裂、吕蒙白衣渡江、刘备伐吴失败及夷陵惨败。正史中孙权仅要求刘备交还部分地区，刘备不乐意，孙权派兵夺取荆南三郡；曹操攻占汉中后，刘备回师救援西川，与孙权签订湘水划界（湘水之盟）。
-- **主持人**：单刀赴会实为鲁肃与关羽不带兵士在中立区谈判，被罗贯中美化。
-- **发言人2**：白衣渡江伪装商人打仗突破底线，开了坏头。
-### 东吴大都督命运与蜀汉内斗
-- **主持人**：列举东吴大都督结局——周瑜正史被曹人射毒箭阵亡，鲁肃因瘟疫病故，吕蒙病故，陆逊因二宫之争被孙权活活逼死。
-- **发言人2**：蜀汉也存在内斗。
-- **主持人**：刘禅放权诸葛亮，姜维因是魏国降将缺乏说服力；魏延正史没有谋反，但烧毁栈道，行为与谋反无异。
-### 三顾茅庐与隆中对
-- **发言人5**：刘备屡战屡败后经推荐三次拜访诸葛亮，第三次见到并提出隆中对。
-- **主持人**：隆中对战略为横跨荆益、外结好孙权、西和诸戎、南抚夷越，趁魏国变动北伐；白衣渡江后蜀汉失去荆州全境，横跨荆益策略不成立，诸葛亮北伐目标转向关中陇西，第一次北伐因马谡失街亭失败，后期北伐成为绝望抗争。
-### 红楼梦版本与判词解读
-- **发言人4**：《红楼梦》有多种解读角度，可当爱情小说看，巧在未解之谜。
-- **发言人3**：前八十回为曹雪芹所写，后四十回为高鹗续写。
-- **发言人4**：高鹗续本总体合理，但反复读前八十回后会察觉林黛玉性格变化。
-- **发言人3**：第五回贾宝玉梦游太虚幻境以判词形式交代结局，但未明确点出探春、史湘云等结局，存在猜测空间。
-- **发言人3**：晴雯性格像林黛玉，袭人性格像薛宝钗，晴雯之死为曹雪芹原作所写。
-### 红楼梦解读与版本选择
-- **发言人2**：有人解读林黛玉代表明朝、薛宝钗代表清朝。
-- **发言人4**：秦可卿被解读为前朝公主；金陵十二钗判词在第五回出现，正钗对应小姐、副钗对应丫鬟。
-- **发言人2**：询问为何选高鹗后四十回作为官方结尾。
-- **发言人4**：高鹗续本总体合理，官方说法为未违背作者原意。
-- **发言人3**：提及北京植物园附近的曹雪芹小道。
-## 共识与分歧
-### 达成共识
-- **三国内容价值判断**：三国故事到诸葛亮去世已基本完成主体部分，后续内容吸引力下降。
-- **白衣渡江评价**：伪装商人打仗突破道德底线，开了坏头。
-- **隆中对战略失效**：白衣渡江后蜀汉失去荆州全境，横跨荆益策略不再成立。
-- **红楼梦版本归属**：前八十回为曹雪芹所写，后四十回为高鹗续写。
-- **高鹗续本定位**：总体合理，官方说法为未违背作者原意，可作为官方结尾。
-### 主要分歧
-- **刘备称王责任归属**：主持人认为刘备贸然称汉中王引发连锁反应，导致孙刘联盟破裂；发言人2未直接反驳，但将批评焦点放在白衣渡江的作战方式上，认为其突破底线。
-- **红楼梦人物解读**：存在林黛玉代表明朝、薛宝钗代表清朝、秦可卿为前朝公主等解读，发言人4指出判词未明确点出探春、史湘云等结局，存在猜测空间，各方未形成统一解读。
-## 未决问题
-- **红楼梦人物结局**：判词未明确点出探春、史湘云等人物结局，存在猜测空间，需结合文本进一步研判。
-- **红楼梦政治隐喻解读**：林黛玉代表明朝、薛宝钗代表清朝、秦可卿为前朝公主等解读方向尚未验证，需对照文本细节考证。</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>6453/1859</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="13.5" customHeight="1" s="9">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 好，刚才咱们讲完那个《红楼梦》、还有《三国》、《水浒》、《西游记》和《金瓶梅》，然后咱们继续延伸着三国那个接下来的故事线走。然后咱们从那个兵法和战法角度来考虑，大家认为赤壁之战的影响主要是体现在哪一方面？就是这样的。
 发言人 2  00:00:22
 这咋说呀，也不好说吧。
@@ -15857,60 +12491,9 @@
 这地盘太小了。
 发言人 1  00:15:15
 差不多了差不多了差不多了。行，咱们这一条先停一下。下一张是什么。</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>小组讨论</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t># 三国关键战役与武将能力研讨
-## 讨论议题
-本次会议围绕三国历史中的关键战役与人物展开研讨，由主持人引导，参与者以互动问答方式推进。讨论重点分析了赤壁之战、合肥之战、火烧连营等战役的战术得失，并对孙权、关羽、陆逊等武将的军事能力进行了评价。整体氛围轻松，属于历史话题的闲聊式交流。讨论中形成了若干对历史定论的重新审视：赤壁之战曹操失败源于不擅水战，合肥之战孙权失败源于不擅陆战；孙权军事才能受到多方质疑，被调侃为"合肥战神孙十万"；关羽能力获认可但归因于队友不配合；诸葛亮北伐受限于蜀汉地盘太小。讨论最终未形成正式决策，以观点交流与历史解读为主。
-## 发言要点
-### 赤壁之战与合肥之战
-- **发言人 1**：赤壁之战曹操失败并非实力不济，而是其军队以虎豹骑等骑兵为主，擅长陆战，缺乏水军，无法在长江水域与东吴抗衡。东吴以水军见长，擅长划船、游泳等水上作战，但陆战能力不足。
-- **发言人 1**：这一水陆差异在合肥之战中再次显现。孙权动员所有武将进攻合肥，但面对张辽、李典、乐进三员大将镇守的城池，吴军因不擅陆战而大败。公元215年，张辽率800死士冲击孙权军队，孙权大败，史称"张八百大破孙十万"。
-- **发言人 1**：合肥是东吴北伐的必经之地，孙权一生多次进攻均未成功。
-### 孙权军事才能的讨论
-- **发言人 2、发言人 3**：孙权军事才能差，多次战败。除合肥之战外，早期曾以数万人被刘繇数千人击败，打仗表现不佳。
-- **发言人 1**：补充细节——孙权在合肥之战中差点被张辽俘虏，因张辽等人不认识孙权而错失机会。后人调侃孙权为"合肥战神孙十万"，认为其正面作战常败，但善于偷袭盟友。
-- **发言人 1**：孙权墓位于南京紫金山，但确切位置已不可考，墓前立碑，游客常放置张辽的卡片以示调侃。
-### 火烧连营与陆逊评价
-- **发言人 1**：刘备因体恤士兵在密林扎营，被陆逊抓住秋季干燥时机，火烧连营七百里，刘备只身逃回白帝城。
-- **发言人 2**：提及陆逊与孙家有仇。
-- **发言人 1**：解释陆逊为江东四杰之一，并讨论孙策被刺杀及孙权守成能力。引用曹操评价"生子当如孙仲谋"，认为孙权虽开疆拓土能力不足，但能守住家业。
-### 武将能力比较与北伐讨论
-- **发言人 1**：关羽能力很强，有斩颜良、水淹七军等战绩，失败是因为队友不争气，而非能力不行。
-- **发言人 3**：关羽阵中斩将是历史第一人；黄忠在定军山斩夏侯渊，但方式与关羽不同。
-- **发言人 1**：诸葛亮第一次北伐若用魏延守街亭可能成功，但蜀汉地盘太小，难以支撑。
-## 共识与分歧
-### 达成共识
-- **赤壁之战与合肥之战的败因归因**：曹操因不擅水战而败于赤壁，孙权因不擅陆战而败于合肥，水陆作战能力差异是两场战役的关键因素。
-- **孙权军事才能有限**：孙权多次北伐合肥未果，正面作战常败，其军事才能受到普遍质疑。
-### 主要分歧
-- **关羽战败的归因**：发言人 1 认为关羽能力很强，失败是因为队友不争气；讨论中未出现对此结论的明确反对意见，但发言人 3 补充了关羽阵中斩将等战绩作为能力佐证。
-- **孙权守成能力的评价**：发言人 1 引用曹操评价，认为孙权虽开疆拓土能力不足，但能守住家业；发言人 2、发言人 3 则侧重强调孙权多次战败的事实，对其能力整体持否定态度。
-## 未决问题
-- **诸葛亮北伐的替代方案**：若用魏延守街亭是否可能成功，讨论中提出此假设但未深入验证；蜀汉地盘太小被认定为根本制约因素，无明确跟进意向。
-- **孙权墓的确切位置**：位于南京紫金山但确切位置已不可考，仅作为讨论中的补充信息，无进一步考证计划。</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>4899/1559</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="13.5" customHeight="1" s="9">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 咱们讲一下阿富汗战争，也就是1979年到1989年的苏联入侵阿富汗战争，史称苏阿战争。阿富汗在亚洲的中部，也就是今天呃的差不多新疆往西再出去瓦汉走廊之后到达阿富汗腹地，其国家东接中国，北邻塔吉克斯坦，南接。巴基斯坦、锡林、伊朗，也被称为亚洲的中间走廊地带，是名副其实的兵家必争之地。在历史上，各大列强都对阿富汗有一个觊觎之心，但是其国土纵深百分之九十都为高原山地地带，也是名副其实的。易守难攻的地带从历史上列强入侵哈。阿富汗以及后来的结果来看，阿富汗多次获得其帝国坟场的称号。第一次大英帝国入侵了之后，短暂的时期被阿富汗给反推回巴基斯坦地区；第二次，也就是我们今天要说的苏联入侵阿富汗这么一个状态。
 发言人 1  00:01:26
 阿富汗当时在一二十世纪50年代的时候，它是同时与苏联以及西方国家保持一个友好交往的一个状态。它主要实行的一个制度就还是以那个就是君主立宪制为基准模板进行的，同时就是其国内精英阶层和知识界阶层也是奉行着亲英与亲苏两头政策的，进并行。在文化上，积极向英国这一块的靠拢。就比如说是英国的议会制度、君主立宪制度以及大学现代科学的承办，师从英国；但是国家建设和工业方面又向苏联看齐，然后由地缘上引发的原因。导致这个国家，它跟西方国家和苏联的关系都不差。
@@ -15956,66 +12539,9 @@
 下一个问题。
 发言人 2  00:11:25
 雨翔，你刚才说了吗？说了说了是吧？第一个问题，ok那咱咱们差不多了，我一直在说行，咱们差不多了，可以关上了。11分钟够不够够10到15分钟都行，然后下一场是啥？下一场是女生说。</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>专题讲座</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t># 苏阿战争历史背景、过程与影响研讨会
-## 讲座概况
-本次研讨会由主讲人系统讲解1979年至1989年苏联入侵阿富汗的苏阿战争，围绕阿富汗的地理战略位置、苏联出兵原因、战争过程及最终撤军结果展开，并解答听众关于阿富汗战略价值、资源状况、圣战者含义及战争难打原因等疑问。主讲人指出，阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，是兵家必争之地；其国土纵深百分之九十为高原山地，易守难攻，历史上多次获得"帝国坟场"称号。主讲人强调，苏联出兵阿富汗是冷战苏攻美守时期意识形态扩张与军事霸权恐吓的结果，最终苏联在阿富汗人民战争的消耗下于1989年撤军。讲座核心逻辑框架为：先交代阿富汗地理与历史背景，再梳理苏联入侵前的国内局势与出兵过程，继而展开国际反应与十年游击战争，最后以撤军收束并回应听众疑问。
-## 核心观点
-### 阿富汗是兵家必争的"帝国坟场"
-- **地理战略位置关键**：阿富汗位于亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，是兵家必争之地。
-- **地形易守难攻**：国土纵深百分之九十为高原山地地带，易守难攻。
-- **历史先例佐证**：历史上大英帝国入侵阿富汗后曾被反推回巴基斯坦地区，阿富汗由此获得"帝国坟场"称号。
-### 苏联出兵是冷战思维与阿明亲美共同作用的结果
-- **战前阿富汗两面外交**：20世纪50年代阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，国内精英奉行亲英与亲苏两头政策，文化上师从英国，国家建设和工业方面向苏联看齐。
-- **阿明亲美引发苏联不满**：基辛格评价阿富汗国王阿明"用苏联的火柴点美国的香烟"，形容其两面讨好的墙头草姿态。后来阿明因对苏联干涉内政不满并过度导向美国，引发苏联领导层不满。
-- **冷战大背景催化**：同时期冷战状态是苏攻美守，苏联咄咄逼人进行意识形态扩张以及军事霸权恐吓，共同导致出兵阿富汗。
- - 根据勃列日涅夫逻辑，不允许苏联大家庭成员外出，因此苏联必须出兵阿富汗，加上阿富汗的战略要地，导致苏联战略性失误。
-- **出兵过程**：1979年12月24日平安夜，苏联以兵变政变形式，借口阿富汗请求救援，从东部、中部及西部（塔吉克斯坦、土库曼斯坦方向）分路突入，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营。
-### 国际合力援助下的十年游击战拖垮苏联
-- **多国联合反苏**：苏联入侵招致众多阿拉伯国家、中国及西方盟国的不满，各方合力援助阿富汗。
-- **分工协作抵抗**：阿富汗和穆斯林国家出动兵源，中国和西方盟国提供武器与情报资源，共同支持阿富汗抵抗组织。
-- **中国援助细节**：中国曾援助阿富汗圣战者，教授地道战、地雷战等战法，并提供五六式冲锋枪和五六式半自动步枪。
-- **美国援助细节**：美国援助了毒刺防空导弹，有效压制苏联的雌鹿武装直升机。
-- **战争结果**：游击战争持续十年，最终苏联于1989年从阿富汗撤军。
-## 金句总结
-&gt; "用苏联的火柴点美国的香烟。"
-&gt; —— **主讲人**（讲到基辛格对阿富汗国王阿明两面讨好姿态的评价时）
-&gt; "根据这个勃列日涅夫的这个逻辑来说，是不允许任何一个成员外出的。"
-&gt; —— **发言人 3**（讨论苏联出兵阿富汗是冷战思维下的必然选择时）
-&gt; "同时期冷战的状态也是苏攻美守时期，然后苏联咄咄逼人的进行意识形态的扩张以及军事霸权的恐吓。"
-&gt; —— **主讲人**（论证苏联出兵是冷战苏攻美守时期意识形态扩张和军事恐吓的结果时）
-## Q&amp;A 环节
-**发言人 2**：阿富汗的战略价值体现在哪些方面？
-**主讲人**：阿富汗地处亚洲中间走廊地带，是兵家必争之地；其国土纵深百分之九十为高原山地，易守难攻，历史上多次获得"帝国坟场"称号。
-**发言人 2**：阿富汗的石油资源状况如何？
-**主讲人**：阿富汗是贫油国，但周边国家如伊朗、土库曼斯坦、塔吉克斯坦都是富油国。
-**发言人 2**：圣战者是什么意思？
-**主讲人**：圣战者指具有狂热激进伊斯兰圣战思想、抱着同归于尽思想进行圣战的武装人员。
-**发言人 2**：为什么苏联打这场战争这么难？
-**主讲人**：阿富汗百分之九十地区为高原山地，乡村由部落长老制控制，政府控制力弱，导致列强难以有效控制；地形适合游击战，苏联重装部队难以发挥作用，基层官兵普遍厌战，士气低落。</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3129/1880</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="13.5" customHeight="1" s="9">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 唠呗，就刚才继续呗。
 发言人 2  00:00:02
 中间唠一个哥斯拉的这个讲完了，咱们再讲讲日本其他阴暗的东西，就比如说是那个东野圭吾的白夜行吧。
@@ -16191,64 +12717,9 @@
 可以提问。
 发言人 2  00:15:55
 下一个由主。</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>小组讨论</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t># 多国文学主题与历史背景交流讨论会
-## 讨论议题
-本次讨论会以闲聊形式展开，参与者围绕日本、法国、英国、俄国、美国及中国等国家的文学作品进行交流，重点探讨各国文学的主题特点、底层描写、历史背景与人性批判。讨论从《白夜行》切入，延伸至《菊与刀》《悲惨世界》《古拉格群岛》《假如我是真的》《西游记》等作品，并涉及饥荒、移民、西藏解放等历史话题。整体氛围轻松随意，观点发散，未形成正式决议。
-## 发言要点
-### 日本文学讨论
-- **发言人 1**：《白夜行》作为悬疑小说，叙事手法独特，结局阴暗，符合日本文学对人性阴暗面的刻画。
-- **发言人 2**：美国作家本尼迪克特的《菊与刀》生动描绘了日本人性格特点，《白夜行》体现了日本社会的阴暗面。
-### 法国与英国文学对比
-- **发言人 1**：法国文学具有抗争精神。
-- **发言人 4**：法国小说多描绘底层民众，英国文学多描写贵族生活。
-- **发言人 2**：法国文学具有浪漫理想主义精神，如《悲惨世界》体现了奉献精神。
-### 俄国文学与底层描写
-- **发言人 2**：比较法国和俄国对底层民众的描写，认为俄国文学更注重人性丑恶的揭露与批判，如《古拉格群岛》批判人性黑暗，最早出版法语版，俄语版在苏联解体后发行。俄国在这方面更为讽刺。
-- **发言人 2**：喜欢契诃夫的作品，如《变色龙》《装在套子里的人》《凡卡》；苏联作家格罗斯曼的《命运与生活》以平民视角揭示苏联红军基层的真实形象。
-- **发言人 1**：国内底层文学如《平凡的世界》因政策原因受限。
-### 美国文学与历史背景
-- **发言人 2**：美国文学风格不同于欧洲，更关注现代社会。
-- **发言人 1**：美国历史短，相对幸福。
-- **发言人 2**：北美大平原农业资源丰富，美国从未经历饥荒，因此美国人无法真正理解饥荒为何物。
-### 中国文学与历史事件
-- **发言人 1**：国内底层文学如《平凡的世界》因政策受限。
-- **发言人 2**：台湾电影《假如我是真的》改编自俄国小说《钦差大臣》，结合文革时期知青上山下乡事件，拍摄于上世纪七十年代末八十年代初，用于台湾对大陆的舆论宣传战。
-### 《西游记》与宗教批判
-- **发言人 2**：狮驼岭章节描写佛门三大圣兽（青狮、白象、大鹏）吃光全城百姓，距离灵山仅500公里，与佛教普度众生理念相悖，吴承恩批判佛教作为上层统治工具的本质。联系西藏历史，强调共产党解放西藏的必要性，并指出汉传佛教与藏传佛教的本质区别。
-- **发言人 1**：《黑神话悟空》未设计狮驼岭章节，因过于血腥且意义深刻。
-## 共识与分歧
-### 达成共识
-- **各国文学主题差异**：法国文学体现抗争精神与浪漫理想主义，英国文学多描写贵族生活，俄国文学更注重人性丑恶的揭露与批判，美国文学更关注现代社会。
-- **《西游记》宗教批判**：狮驼岭章节与佛教普度众生理念相悖，吴承恩批判佛教作为统治工具。
-### 主要分歧
-- **底层文学受限程度**：发言人 1 认为国内底层文学因政策原因受限；发言人 2 未对此提出异议，但未深入展开讨论。
-## 未决问题
-- **国内底层文学政策限制**：发言人 1 提到《平凡的世界》等底层小说因政策原因无法观看，但未明确具体限制范围与后续讨论方向。
-- **《黑神话悟空》狮驼岭章节缺失**：发言人 1 提到该游戏未设计狮驼岭章节，因过于血腥且意义深刻，但未进一步探讨游戏改编与原著批判精神的取舍关系。</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>5886/1481</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="13.5" customHeight="1" s="9">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 各位好，咱们今天开个二十分钟的短会，主要是过一下手机图库项目目前的整体进展，顺便对齐下接下来的排期和潜在风险。老规矩，先听下产品侧的交互迭代和用户反馈，然后开发两位同步下技术实现和性能优化的情况，最后我总结一下接下来的重点工作。产品这边先开始吧
 发言人 2  00:00:36
 好的，我这边先同步下。最近两周咱们重点在推智能分类和相册推荐的改版，目前高保真原型已经出了V1.5版，主要调整了网格视图的交互逻辑，把长按手势做了更自然的微动效反馈。不过测试那边反馈说部分低端机上滑列表的时候偶尔会有掉帧的情况，我已经跟开发2沟通过了，看能不能通过降低预览图缩放级别来换帧。另外，用户调研那边收到不少关于‘隐私相册’入口太深的吐槽，我建议下一版直接把入口提到首部顶部二级菜单，产品经理看这个范围变更会不会太大
@@ -16304,76 +12775,9 @@
 好嘞，我十一点半前发你。大家效率拉满，咱们月底见分晓
 发言人 1  00:12:18
 好，那就这样，散会。辛苦各位，有问题随时在飞书上同步</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议为手机图库项目周度进展同步会，产品、开发、测试等多方参与，围绕智能分类与相册推荐改版、AI识别模型性能优化、缩略图渲染卡顿、云同步断点续传、时间轴加载速度等核心议题展开研讨。会议明确了隐私相册入口调整、本地缓存策略、分片加载、端侧预过滤、插件化架构等解决方案，并确定了月底封版、下周三内测包发布等关键节点。产品侧汇报了高保真原型V1.5版进展，开发侧确认AI识别模型V2版准确率提升约88%，同时针对请求耗时上升、弱网同步OOM崩溃、批量删除数据库锁死等问题逐一给出应对方案。会议还就AI修图功能预留接口、性能压测报告等事项达成共识，整体推进有序。
-## 要点梳理
-### 1. 产品侧交互迭代与用户反馈
-- 高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈。
-- 低端机上滑列表偶发掉帧，产品侧建议降低预览图缩放级别以换取帧率稳定。
-- 用户调研反馈隐私相册入口太深，建议提升至首部顶部二级菜单，产品经理认可该调整并要求出交互方案供评审。
-- 掉帧问题需在性能压测前解决，下周进入性能压测阶段。
-### 2. AI智能标签接口与模型部署
-- AI识别模型V2版已跑通，准确率提升约88%，但视频帧提取功能导致单次请求耗时从800ms涨至约1.5s。
-- 异步推送方案被否决，产品侧认为用户点开相册无实时结果会感觉功能卡死，决定采用本地缓存策略，使用CQLite缓存层，开发1下午拉分支，预计三天联调完成。
-- 端侧预过滤方案用轻量级模型先过滤非图片内容，可平均降低耗时一半，需申请200MB本地缓存空间，产品侧评估安装包体积影响后认可。
-- 按需下载方案预计两天完成。
-### 3. 云同步与内存管理问题
-- 云同步断点续传在弱网环境下状态机紊乱，同步队列积压超1000张时部分机型OOM崩溃。
-- 已采用分片加载机制，每次拉取50张。
-- 后台静默同步权限申请被否决，产品经理认为审核严格大概率下不了，决定维持分片加载方案，但要求进度不能拖。
-### 4. 缩略图渲染优化与性能评审准备
-- 新图片解码库将JPEG硬解换为软解，内存占用降约30%，CPU占用上升。
-- 主流三款机型灰度帧率稳定在60帧，低端机约50帧。
-- 批量删除照片时触发回收站重建索引导致数据库锁死Bug，临时方案用消息队列排队处理，正式修复排入V1.2迭代。
-- 周四性能评审，性能报告初稿今晚出。
-### 5. 时间轴加载优化与资源冲突协调
-- 时间轴滑动到二十年前老照片时页面卡死超3秒，原因为历史图片EXIF解析耗时太长和磁盘IO瓶颈。
-- 方案为本地索引预加载，最近三个月照片建树状结构，滑到底部动态加载旧数据。
-- 预加载放主线程IO池，同步放子线程后台服务，互不影响。
-- 预加载需用户授权媒体和存储权限，产品侧设计权限引导弹窗，风格走柔和提示路线，明天出稿。
-### 6. AI修图功能预留与架构规划
-- AI修图功能本次不排期，预留接口和UI占位，开发侧采用插件化架构，渲染层用GLSL统一接口。
-- 管线重构工作量约增加一周，产品经理同意调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化。
-- 开发2需评估精确工作量，今天下班前反馈。
-### 7. 里程碑确认与收尾
-- 月底封版，内测包暂定下周三发布，重点测试AI分类和同步模块。
-- 开发1需与DBA对齐索引策略，优化建表。
-- 性能报告分iOS和安卓对比数据，合并为一份总览。
-## 结论与决定
-- **隐私相册入口**：提升至首部顶部二级菜单，产品经理评审交互方案。
-- **AI识别方案**：采用本地缓存策略，开发1下午拉分支，预计三天联调完成；端侧预过滤方案获认可，按需下载预计两天完成。
-- **云同步方案**：采用分片加载机制，每次拉取50张，不申请后台静默同步权限。
-- **缩略图渲染**：采用新解码库方案，数据库锁死Bug正式修复排入V1.2迭代。
-- **时间轴加载**：采用本地索引预加载，预加载放主线程IO池，同步放子线程后台服务。
-- **AI修图功能**：预留接口和UI占位，开发侧做插件化架构，渲染层用GLSL统一接口。
-- **优先级调整**：非核心UI微调往后排，资源优先给管线重构和AI标签优化。
-- **里程碑**：月底封版，下周三发内测包，重点测试AI分类和同步模块。
-- **性能报告**：分iOS和安卓对比数据，合并为一份总览。</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>3605/1869</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="13.5" customHeight="1" s="9">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 好了，大家都到齐了，手机都放一下啊。今天咱们这个月度研讨会，就定在下午两点到两点四十，一共四十分钟。时间不长，但内容得扎实。上个月的市场波动挺大，咱们这个项目虽然整体去化还行，但有些数据我不满意。组长，你先从整体数据起个头，把核心指标过一遍
 发言人 2  00:00:35
 行，总监。我这边拉了后台的完整数据。上一个月咱们案场总到访是三百二十组，环比增加了百分之十五，这个数据是达标的。但是转化率低了点，成交七十六套，转化率是百分之二十三，比上个月的百分之二十七掉了一个点。渠道带看占比是百分之六十五，自然来访只有百分之三十五。蓄客量目前在三千二百组左右，认购到成交的流失率大概在百分之十八。整体来说，量是够的，但卡在逼定和转化环节
@@ -16443,72 +12847,9 @@
 明白，马上梳理客户
 发言人 5  00:15:07
 好的，我去改话术和准备物料</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次月度研讨会由销售总监主持，时长40分钟，聚焦上月项目去化数据与转化率下滑问题。会议复盘了案场到访、成交、转化率、渠道占比等核心指标，分析了客户流失的两大抗性（价格预期与交付信心），并针对性地制定了工地开放日标准化、逼定权益可视化、渠道带看实名制、周末业主答谢会联动去化、专项培训与销控纪律等多项改进措施。同时明确了本月120套的去化目标及小组任务拆分，并部署了具体执行动作与责任人。上月案场总到访320组，环比增加15%，达标；成交76套，转化率23%，较上月27%下降4个百分点；渠道带看占比65%，自然来访占比35%；蓄客量约3200组，认购到成交流失率约18%。整体量够但转化不足，卡在逼定和转化环节。本月总去化目标120套，比上月多50%，任务拆分至各销售小组，并配套专项培训、销控纪律与财务法务支持。
-## 要点梳理
-### 1. 上月销售数据复盘
-- 上月案场总到访320组，环比增加15%，达标；成交76套，转化率23%，较上月27%下降4个百分点。
-- 渠道带看占比65%，自然来访占比35%；蓄客量约3200组，认购到成交流失率约18%。
-- 整体量够但转化不足，卡在逼定和转化环节；渠道带看比例偏高，反映自主拓客能力和案场拦截能力退化。
-### 2. 客户流失原因分析
-- 客户流失主要集中在价格预期和交付信心两大抗性。
- - 价格预期：竞品推特价房、首付分期、送物业费等策略，客户心理有落差。
- - 交付信心：客户对园林选材、地下车库层高、外墙保温层等细节关注度高，怕买错。
-- 工地开放日频率不够，流程繁琐，报备审批需半天，影响客户实地考察与转化。
-### 3. 逼定策略与权益可视化
-- 针对价格抗性，销冠采用"算总账"方法，对比单价高2000元但十年省物业和维修费，并配合"限时权益"逼定函，本周定可申请多送三年物业费。
-- 销售B提出权益具象化建议，将三年缴费明细打印放在合同旁，增强客户信任；同时指出案场逼定函物料更新慢，常使用上个月版本。
-- 组长承诺本周联系设计出新版物料，并制作"权益可视化"台卡。
-### 4. 跟进节奏与渠道管理
-- 总监强调"客户不过夜"原则，要求提速跟进。
-- 安排组长带销售A和销售B回访上周未成交的300多组客户，重点盯"再考虑考虑"的；销冠梳理手头20多个高意向客户，周末集中逼定。
-- 渠道带看量高但无效带看多，决定实施实名登记和需求标签制度，否则扣减渠道积分；总监负责与渠道部沟通，强调质量大于数量，若渠道带看质量不行直接换备选。
-- 销售A担心查太严得罪中介，总监坚持底线不妥协。
-### 5. 老带新政策与业主答谢会
-- 老带新政策：成功一套奖励2万现金或等值车位券，销售B本月推了4组，2组在谈。
-- 组长准备定制伴手礼（高端茶叶礼盒、定制保温杯）；销冠建议搞"业主推荐官"活动，成功推荐可升级物业服务等级（优先维修、免费家政清洗），软硬结合，组长下周前出详细执行表。
-- 周末举办业主答谢会，统一话术为"老业主专属品鉴宴"，避开"促销"字眼；销售B主抓流程，销售A负责邀约和逼定记录，销冠带人协助，联动高意向客户集中去化。
-### 6. 目标分解与执行部署
-- 本月总去化目标120套，比上月多50%；任务拆分：销冠28套，组长+销售A+销售B共50套，剩余12套机动。
-- 本周安排两次专项演练："竞品对比与抗性化解"、"逼定时机与谈判心理学"，课后现场抽考，结果挂钩绩效系数。
-- 销控必须实时同步，CRM系统锁房，出问题直接问责；组长设置专人每小时刷新销控大屏。
-- 财务和法务周末轮流值班在案场外围，现场出数出收据，预计成交率提升至少两成。
-- 散会后半小时内组长发会议纪要和任务分解表到工作群。
-## 结论与决定
-- **工地开放日标准化**：定于每周三下午固定开放，提前两天在CRM系统推送意向客户，客户直接对接专属顾问，不走复杂流程。
-- **逼定权益可视化**：本周内更新物料，制作"权益可视化"台卡，将三年缴费明细等权益具象化呈现。
-- **渠道带看实名制**：实施实名登记，必须有明确需求标签，否则扣减渠道积分；总监负责与渠道部沟通，坚持质量大于数量。
-- **周末业主答谢会**：统一话术为"老业主专属品鉴宴"，销售B主抓流程，销售A负责邀约和逼定记录，销冠带人协助。
-- **本月去化目标**：总目标120套，销冠28套，组长+销售A+销售B共50套，剩余12套机动。
-- **专项培训**：本周安排两次专项演练，课后现场抽考，结果挂钩绩效系数。
-- **销控纪律**：销控必须实时同步，CRM系统锁房，出问题直接问责；组长设置专人每小时刷新销控大屏。
-- **财务法务支持**：周末轮流值班在案场外围，现场出数出收据，预计成交率提升至少两成。
-- **会后动作**：散会后半小时内组长发会议纪要和任务分解表到工作群。</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>4211/2045</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="13.5" customHeight="1" s="9">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>发言人 1  00:00:00
+  </si>
+  <si>
+    <t>发言人 1  00:00:00
 好了，人都齐了，咱们直接开。今天主要是过一下上周ASR模型的迭代进度，还有线上推理延迟和那个长音频卡死的问题。A和B先分别同步下各自负责板块的现状，有什么卡点或者需要协调的资源，现在直接提，别留到后面
 发言人 2  00:00:19
 嗯嗯，收到。组长，我先从数据和模型训练这块汇报。上周咱们定好的混合语料库，数据清洗流水线已经跑完了第二轮。我把那些长尾噪音、极端口音和背景人声重叠的片段单独做了分流，现在数据集里有效的语音时长占比从之前的89%提到了94%左右。另外，标注对齐这块，我重新校对了CTC的blank token分布，发现之前多音字和连读场景的切分点确实有点偏，这周打算用新基准跑一轮消融
@@ -16568,182 +12909,1631 @@
 没了，我这边就是模型训练、数据对齐和自动化评估，按节奏走就行。周三前把CI脚本和测试用例发群里评审
 发言人 3  00:11:57
 也没问题，推理优化、VAD消融、热修复和监控文档我盯着。组长，那咱们今天先到这？辛苦大家</t>
-        </is>
+  </si>
+  <si>
+    <t>MOS分</t>
+  </si>
+  <si>
+    <t>模板准确性</t>
+  </si>
+  <si>
+    <t>竞品对比</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>自定义模板</t>
+  </si>
+  <si>
+    <t>智能识别</t>
+  </si>
+  <si>
+    <t>新闻发布</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>沟通交流会</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>总结复盘会</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用纪要</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作研讨会</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>庭审记录</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目进度会</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>课堂记录</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识笔记</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>采访记录</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>就医咨询</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>面试报告</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>参观游览</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>调研访谈</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>家校沟通</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>团队例会</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>专题讲座</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>辩论会</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品发布</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>政府报告</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>小组讨论</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话记录</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B56"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="55.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="56.125" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="5" t="s">
+        <v>89</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>通用纪要</t>
-        </is>
+      <c r="B1" s="5" t="s">
+        <v>90</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t># 通用纪要
-## 全文摘要
-本次会议围绕ASR模型迭代进度、线上推理延迟波动及长音频解码卡死问题展开。数据侧完成混合语料库第二轮清洗，有效语音时长占比从89%提升至94%，验证集WER下降0.8个点；模型侧计划从全Transformer架构转向流式RNN-T与Transformer混合架构，并引入INT8量化以降低显存占用。推理侧针对动态Batching导致的首字延迟波动，提出静态分段加流式解码方案，目标首字延迟控制在80ms以内，吞吐量稳定在120路并发。针对长音频卡死问题，决定加入early stopping机制和超时熔断，优先保障稳定性。会议还明确了CI自动评估流水线、监控面板建设、前端32k采样率升级等事项，并落实各项任务的责任人与时间节点。
-## 要点梳理
-### 1. 数据清洗与模型训练进展
-- 数据清洗流水线完成第二轮，长尾噪音、极端口音及背景人声重叠片段被单独分流，有效语音时长占比从89%提升至94%。
-- 标注对齐环节重新校对CTC的blank token分布，发现多音字和连读场景切分点存在偏差，计划用新基准跑消融。
-- 针对低资源语言混合边界场景的切分毛刺，尤其是中英文切换时过渡音被吞或重复解码的问题，计划将全Transformer架构改为流式RNN-T与Transformer混合架构，先在20小时核心数据上训练。
-- 数据增强策略增加时间偏移，并计划引入MixUp和Cut以提升对背景白噪声和混响的鲁棒性。
-- RNN-T的prefix LM缓存计划做INT8量化，配合动态缓存释放策略，预计降低30%左右显存占用，具体压测数据待补充。
-### 2. 推理延迟优化与动态Batching调整
-- 动态Batching在长短音频混排时导致首字延迟波动在150ms至300ms之间，产品反馈体验不连贯。
-- 计划改为静态分段加流式解码方案：音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，目标首字延迟控制在80ms以内，吞吐量稳定在120路并发。
-- VAD预过滤阈值当前为-25dB，结合能量和谱熵双模型判断，但真实线上环境底噪复杂，计划拉取线上流量回放做端到端对比。
-- 组长要求VAD阈值通过消融实验平衡误切率和漏切率，并强调流式架构切换不能影响现有非流式离线批处理，测试用例需覆盖全。
-- 算力方面，组长协调下周一开始划拨三块A100用于增量训练，需错峰使用，避免与NLP组任务冲突。
-### 3. 长音频卡死问题与热修复方案
-- 线上出现用户输入超长连续且带方言口音音频时，解码器陷入无效循环导致服务器节点重启。
-- 解码器默认max steps为2048个token，超时时间5秒，但部分音频解码序列长度超阈值后未做优雅降级，直接报OOM；日志显示RNN-T的attention权重震荡不收敛。
-- 计划加入early stopping机制：连续30步置信度低于0.2时强制截断并返回当前序列，同时增加超时熔断和降级返回。
-- 组长决定稳定性优先，精度次之，下周出热修复版本上灰度，并强调训练时注意长序列数据配比，避免全塞短音频。
-### 4. CI自动评估流水线与监控面板建设
-- 计划用GitLab CI实现模型评估自动化，代码合入触发数据拉取、模型加载、测试集解码、结果对比，若WER未下降或RTF超标则直接打回。
-- 评估脚本和流水线配置预计三天完成，周四前出V1版本；推理侧压测数据输出为标准JSON格式，便于流水线直接读取。
-- 监控面板计划接入Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率等指标。
-- 告警阈值分P0和P1两级：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增；监控指标定义文档明天下班前提交，运维对接由组长协调。
-### 5. 前端采样率升级与资源协调
-- 前端SDK采样率16k与新模型32k输入不匹配，上采样引入高频伪影影响识别率；32k模型在长尾词上WER比16k好0.5%。
-- 组长决定推动前端升级，必要时服务端加实时重采样模块兼容。
-- 推理侧负责人担心服务端加模块增加推理链路过长和整体延迟，建议先用libresample写轻量级重采样插件实测CPU占用和延迟影响，CPU开销控制在5%以内再提方案。
-- 组长将拉会推进前端升级，并考虑服务端重采样方案。
-## 结论与决定
-- 流式RNN-T混合架构和2秒切分方案由数据与模型训练负责人和推理侧负责人分头推进，本周五前出详细设计和压测数据。
-- VAD阈值和长序列解码卡死问题，推理侧负责人周四出消融报告和热修复方案，数据与模型训练负责人配合长序列数据配比和评估流水线对接。
-- 前端32k采样率升级，推理侧负责人出对比文档和重采样插件实测，组长拉会推进。
-- 监控面板和CI自动评估流水线，本周内定稿并开始对接运维和测试环境。
-- 解码器加入early stopping机制，连续30步置信度低于0.2时强制截断并返回当前序列。
-- 热修复版本优先保稳定性，下周出灰度版本。
-- CI自动评估流水线由数据与模型训练负责人负责，预计三天完成，周四前出V1版本。
-- 监控面板告警阈值分P0和P1两级，P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增。</t>
-        </is>
+    </row>
+    <row r="2" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
       </c>
-      <c r="D56" s="10" t="n">
-        <v>62.7</v>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>3912/2210</t>
-        </is>
+    </row>
+    <row r="3" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="3">
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>准确性</t>
-        </is>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="D3" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>相关性</t>
-        </is>
+      <c r="E3" t="s">
+        <v>1</v>
       </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>通顺性</t>
-        </is>
+      <c r="F3" t="s">
+        <v>2</v>
       </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>其它问题</t>
-        </is>
+      <c r="G3" t="s">
+        <v>3</v>
       </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>MOS分</t>
-        </is>
+      <c r="H3" s="1" t="s">
+        <v>59</v>
       </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>模板准确性</t>
-        </is>
+      <c r="I3" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>竞品对比</t>
-        </is>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B4" s="8" t="s">
+        <v>61</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="C4" s="1" t="s">
+        <v>62</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4" t="e">
         <f>AVERAGE(竞品对比!#REF!)</f>
-        <v/>
+        <v>#REF!</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" t="e">
         <f>AVERAGE(竞品对比!#REF!)</f>
-        <v/>
+        <v>#REF!</v>
       </c>
-      <c r="F4" s="0">
+      <c r="F4" t="e">
         <f>AVERAGE(竞品对比!#REF!)</f>
-        <v/>
+        <v>#REF!</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="3" t="e">
         <f>COUNTIF(竞品对比!#REF!,-5)/COUNTIF(竞品对比!#REF!,"&lt;&gt;")</f>
-        <v/>
+        <v>#REF!</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4" t="e">
         <f>AVERAGE((竞品对比!#REF!+竞品对比!#REF!+竞品对比!#REF!)/3+竞品对比!#REF!)</f>
-        <v/>
+        <v>#REF!</v>
       </c>
     </row>
-    <row r="5">
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B5" s="8"/>
+      <c r="C5" s="1" t="s">
+        <v>63</v>
       </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="G5" s="3"/>
     </row>
-    <row r="6">
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="8"/>
+      <c r="C6" s="1" t="s">
+        <v>64</v>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3"/>
     </row>
-    <row r="7">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>自定义模板</t>
-        </is>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B7" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>智能识别</t>
-        </is>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B8" s="1" t="s">
+        <v>66</v>
       </c>
-      <c r="I8" s="0">
+      <c r="I8" t="e">
         <f>COUNTIF(#REF!,“可用”)</f>
-        <v/>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
   <mergeCells count="1">
     <mergeCell ref="B4:B6"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<autofilters xmlns="https://web.wps.cn/et/2018/main">
+  <sheetItem sheetStid="1">
+    <filterData filterID="AK20210901JXNSXO8261057">
+      <hiddenRange rowFrom="1" rowTo="9"/>
+      <hiddenRange rowFrom="11" rowTo="22"/>
+      <hiddenRange rowFrom="24" rowTo="35"/>
+      <hiddenRange rowFrom="37" rowTo="48"/>
+      <hiddenRange rowFrom="50" rowTo="55"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO15104038">
+      <hiddenRange rowFrom="1" rowTo="1"/>
+      <hiddenRange rowFrom="3" rowTo="3"/>
+      <hiddenRange rowFrom="5" rowTo="14"/>
+      <hiddenRange rowFrom="16" rowTo="16"/>
+      <hiddenRange rowFrom="18" rowTo="27"/>
+      <hiddenRange rowFrom="29" rowTo="29"/>
+      <hiddenRange rowFrom="31" rowTo="40"/>
+      <hiddenRange rowFrom="42" rowTo="42"/>
+      <hiddenRange rowFrom="44" rowTo="53"/>
+      <hiddenRange rowFrom="55" rowTo="56"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO2962640"/>
+    <filterData filterID="AK20210901JXNSXO16551897"/>
+    <filterData filterID="AK20210901JXNSXO14573183"/>
+    <filterData filterID="AK20210901JXNSXO14760968"/>
+    <filterData filterID="AK20210901JXNSXO16981454"/>
+    <filterData filterID="AK20210901JXNSXO15978846">
+      <hiddenRange rowFrom="1" rowTo="12"/>
+      <hiddenRange rowFrom="14" rowTo="25"/>
+      <hiddenRange rowFrom="27" rowTo="38"/>
+      <hiddenRange rowFrom="40" rowTo="51"/>
+      <hiddenRange rowFrom="53" rowTo="55"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO12102127">
+      <hiddenRange rowFrom="1" rowTo="10"/>
+      <hiddenRange rowFrom="12" rowTo="23"/>
+      <hiddenRange rowFrom="25" rowTo="36"/>
+      <hiddenRange rowFrom="38" rowTo="49"/>
+      <hiddenRange rowFrom="51" rowTo="55"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO17933749">
+      <hiddenRange rowFrom="5" rowTo="5"/>
+      <hiddenRange rowFrom="15" rowTo="15"/>
+      <hiddenRange rowFrom="17" rowTo="18"/>
+      <hiddenRange rowFrom="28" rowTo="28"/>
+      <hiddenRange rowFrom="30" rowTo="31"/>
+      <hiddenRange rowFrom="41" rowTo="41"/>
+      <hiddenRange rowFrom="43" rowTo="44"/>
+      <hiddenRange rowFrom="54" rowTo="54"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO18734464">
+      <hiddenRange rowFrom="1" rowTo="4"/>
+      <hiddenRange rowFrom="6" rowTo="7"/>
+      <hiddenRange rowFrom="9" rowTo="17"/>
+      <hiddenRange rowFrom="19" rowTo="20"/>
+      <hiddenRange rowFrom="22" rowTo="30"/>
+      <hiddenRange rowFrom="32" rowTo="33"/>
+      <hiddenRange rowFrom="35" rowTo="43"/>
+      <hiddenRange rowFrom="45" rowTo="46"/>
+      <hiddenRange rowFrom="48" rowTo="55"/>
+    </filterData>
+    <autofilterInfo filterID="AK20210901JXNSXO14573183">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO16551897">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO16981454">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO14760968">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO15104038">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="段功宸"/>
+            <customFilter operator="equal" val="江涛"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO2962640">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO17933749">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
+        <filterColumn colId="4">
+          <filters>
+            <filter val="1"/>
+            <filter val="2"/>
+            <filter val="3"/>
+            <filter val="4"/>
+            <filter val="5"/>
+            <filter val="3.5"/>
+            <filter val="4.5"/>
+          </filters>
+        </filterColumn>
+        <filterColumn colId="11">
+          <filters>
+            <filter val="2"/>
+            <filter val="3"/>
+            <filter val="4"/>
+            <filter val="5"/>
+            <filter val="3.5"/>
+            <filter val="4.5"/>
+          </filters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO18734464">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="李腾飞"/>
+            <customFilter operator="equal" val="石晓华"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO12102127">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="余瑞芳"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO15978846">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="钟婉婷"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO8261057">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="武思华"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+  </sheetItem>
+  <sheetItem sheetStid="4">
+    <filterData filterID="AK20210901JXNSXO8261057">
+      <hiddenRange rowFrom="1" rowTo="9"/>
+      <hiddenRange rowFrom="11" rowTo="22"/>
+      <hiddenRange rowFrom="24" rowTo="35"/>
+      <hiddenRange rowFrom="37" rowTo="48"/>
+      <hiddenRange rowFrom="50" rowTo="61"/>
+      <hiddenRange rowFrom="63" rowTo="74"/>
+      <hiddenRange rowFrom="76" rowTo="81"/>
+      <hiddenRange rowFrom="83" rowTo="84"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO15104038">
+      <hiddenRange rowFrom="1" rowTo="1"/>
+      <hiddenRange rowFrom="3" rowTo="3"/>
+      <hiddenRange rowFrom="5" rowTo="14"/>
+      <hiddenRange rowFrom="16" rowTo="16"/>
+      <hiddenRange rowFrom="18" rowTo="27"/>
+      <hiddenRange rowFrom="29" rowTo="29"/>
+      <hiddenRange rowFrom="31" rowTo="40"/>
+      <hiddenRange rowFrom="42" rowTo="42"/>
+      <hiddenRange rowFrom="44" rowTo="53"/>
+      <hiddenRange rowFrom="55" rowTo="55"/>
+      <hiddenRange rowFrom="57" rowTo="66"/>
+      <hiddenRange rowFrom="68" rowTo="68"/>
+      <hiddenRange rowFrom="70" rowTo="85"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO14573183">
+      <hiddenRange rowFrom="1" rowTo="5"/>
+      <hiddenRange rowFrom="7" rowTo="18"/>
+      <hiddenRange rowFrom="20" rowTo="31"/>
+      <hiddenRange rowFrom="33" rowTo="44"/>
+      <hiddenRange rowFrom="46" rowTo="57"/>
+      <hiddenRange rowFrom="59" rowTo="70"/>
+      <hiddenRange rowFrom="72" rowTo="84"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO16551897">
+      <hiddenRange rowFrom="1" rowTo="8"/>
+      <hiddenRange rowFrom="10" rowTo="21"/>
+      <hiddenRange rowFrom="23" rowTo="34"/>
+      <hiddenRange rowFrom="36" rowTo="47"/>
+      <hiddenRange rowFrom="49" rowTo="60"/>
+      <hiddenRange rowFrom="62" rowTo="73"/>
+      <hiddenRange rowFrom="75" rowTo="80"/>
+      <hiddenRange rowFrom="82" rowTo="84"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO17933749"/>
+    <filterData filterID="AK20210901JXNSXO18734464"/>
+    <filterData filterID="AK20210901JXNSXO14760968">
+      <hiddenRange rowFrom="1" rowTo="11"/>
+      <hiddenRange rowFrom="13" rowTo="24"/>
+      <hiddenRange rowFrom="26" rowTo="37"/>
+      <hiddenRange rowFrom="39" rowTo="50"/>
+      <hiddenRange rowFrom="52" rowTo="63"/>
+      <hiddenRange rowFrom="65" rowTo="76"/>
+      <hiddenRange rowFrom="78" rowTo="82"/>
+      <hiddenRange rowFrom="84" rowTo="84"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO16981454"/>
+    <filterData filterID="AK20210901JXNSXO12102127">
+      <hiddenRange rowFrom="1" rowTo="10"/>
+      <hiddenRange rowFrom="12" rowTo="23"/>
+      <hiddenRange rowFrom="25" rowTo="36"/>
+      <hiddenRange rowFrom="38" rowTo="49"/>
+      <hiddenRange rowFrom="51" rowTo="62"/>
+      <hiddenRange rowFrom="64" rowTo="75"/>
+      <hiddenRange rowFrom="77" rowTo="84"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO15978846">
+      <hiddenRange rowFrom="1" rowTo="12"/>
+      <hiddenRange rowFrom="14" rowTo="25"/>
+      <hiddenRange rowFrom="27" rowTo="38"/>
+      <hiddenRange rowFrom="40" rowTo="51"/>
+      <hiddenRange rowFrom="53" rowTo="64"/>
+      <hiddenRange rowFrom="66" rowTo="77"/>
+      <hiddenRange rowFrom="79" rowTo="83"/>
+    </filterData>
+    <autofilterInfo filterID="AK20210901JXNSXO15104038">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="段功宸"/>
+            <customFilter operator="equal" val="江涛"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO16551897">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="王俊凯"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO14573183">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="潘奕利"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO17933749">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO18734464">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO14760968">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="翟雨实"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO16981454">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO12102127">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="余瑞芳"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO15978846">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="钟婉婷"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO8261057">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="武思华"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+  </sheetItem>
+  <sheetItem sheetStid="3">
+    <filterData filterID="AK20210901JXNSXO15104038">
+      <hiddenRange rowFrom="1" rowTo="1"/>
+      <hiddenRange rowFrom="3" rowTo="3"/>
+      <hiddenRange rowFrom="5" rowTo="14"/>
+      <hiddenRange rowFrom="16" rowTo="16"/>
+      <hiddenRange rowFrom="18" rowTo="27"/>
+      <hiddenRange rowFrom="29" rowTo="29"/>
+      <hiddenRange rowFrom="31" rowTo="40"/>
+      <hiddenRange rowFrom="42" rowTo="42"/>
+      <hiddenRange rowFrom="44" rowTo="53"/>
+      <hiddenRange rowFrom="55" rowTo="55"/>
+      <hiddenRange rowFrom="57" rowTo="66"/>
+      <hiddenRange rowFrom="68" rowTo="68"/>
+      <hiddenRange rowFrom="70" rowTo="79"/>
+      <hiddenRange rowFrom="81" rowTo="81"/>
+      <hiddenRange rowFrom="83" rowTo="85"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO8261057"/>
+    <filterData filterID="AK20210901JXNSXO14760968"/>
+    <filterData filterID="AK20210901JXNSXO18734464">
+      <hiddenRange rowFrom="1" rowTo="3"/>
+      <hiddenRange rowFrom="5" rowTo="16"/>
+      <hiddenRange rowFrom="18" rowTo="29"/>
+      <hiddenRange rowFrom="31" rowTo="42"/>
+      <hiddenRange rowFrom="44" rowTo="55"/>
+      <hiddenRange rowFrom="57" rowTo="68"/>
+      <hiddenRange rowFrom="70" rowTo="81"/>
+      <hiddenRange rowFrom="83" rowTo="85"/>
+    </filterData>
+    <filterData filterID="AK20210901JXNSXO17933749"/>
+    <filterData filterID="AK20210901JXNSXO15978846"/>
+    <filterData filterID="AK20210901JXNSXO16981454"/>
+    <filterData filterID="AK20210901JXNSXO12102127"/>
+    <filterData filterID="AK20210901JXNSXO14573183"/>
+    <filterData filterID="AK20210901JXNSXO16551897"/>
+    <autofilterInfo filterID="AK20210901JXNSXO15104038">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="段功宸"/>
+            <customFilter operator="equal" val="江涛"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO18734464">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L86">
+        <filterColumn colId="1">
+          <customFilters>
+            <customFilter operator="equal" val="江涛"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+  </sheetItem>
+  <sheetItem sheetStid="12">
+    <filterData filterID="AK20210901JXNSXO17933749">
+      <hiddenRange rowFrom="3" rowTo="3"/>
+      <hiddenRange rowFrom="6" rowTo="9"/>
+      <hiddenRange rowFrom="16" rowTo="19"/>
+      <hiddenRange rowFrom="24" rowTo="28"/>
+      <hiddenRange rowFrom="30" rowTo="31"/>
+      <hiddenRange rowFrom="34" rowTo="39"/>
+      <hiddenRange rowFrom="42" rowTo="42"/>
+      <hiddenRange rowFrom="44" rowTo="47"/>
+      <hiddenRange rowFrom="51" rowTo="52"/>
+      <hiddenRange rowFrom="54" rowTo="57"/>
+      <hiddenRange rowFrom="68" rowTo="69"/>
+      <hiddenRange rowFrom="71" rowTo="71"/>
+      <hiddenRange rowFrom="74" rowTo="74"/>
+      <hiddenRange rowFrom="77" rowTo="81"/>
+      <hiddenRange rowFrom="86" rowTo="86"/>
+      <hiddenRange rowFrom="88" rowTo="91"/>
+      <hiddenRange rowFrom="93" rowTo="94"/>
+      <hiddenRange rowFrom="97" rowTo="103"/>
+      <hiddenRange rowFrom="105" rowTo="105"/>
+      <hiddenRange rowFrom="107" rowTo="110"/>
+      <hiddenRange rowFrom="112" rowTo="116"/>
+      <hiddenRange rowFrom="118" rowTo="118"/>
+      <hiddenRange rowFrom="121" rowTo="123"/>
+    </filterData>
+    <autofilterInfo filterID="AK20210901JXNSXO17933749">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F125">
+        <filterColumn colId="5">
+          <filters>
+            <filter val="1.1：候选人概况中&quot;面试官主要来自权哥、帅总、郑总等&quot;中&quot;郑总&quot;在原文中未明确出现，原文仅出现&quot;权哥&quot;&quot;帅总&quot;及&quot;另一个面试官&quot;，&quot;郑总&quot;为模型推测；2.1：原文中发言者4也参与了部分技术提问（如数据库优化、Nginx跨域），模型未在面试官介绍中体现其角色"/>
+            <filter val="2.1:对'家庭氛围压抑'这一背景信息提炼略浅；3.1:个别标点略不规范"/>
+            <filter val="识别模板为家校沟通,原文为沟通交流会但内容为家长会,家校沟通可适用但与沟通交流会模板略有偏差。2.1:对'青春期沟通'核心话题提炼略浅；3.1:个别标点略不规范"/>
+            <filter val="1.1 提取错误：原文，公司写的12-17k，候选人要15K，公司最高给12，如果13候选人可接受继续后续面试&#10;2.1 细节遗漏：遗漏候选人对自动化测试缺点、动态元素定位的细节描述，做了整体总结"/>
+            <filter val="1.3：摘要中“候选人自称目前是应届生身份”与原文不符，发言者2在自我介绍中明确表示“目前是22岁”，但并未自称“应届生”，而是直接以应聘者身份参与面试，且面试官也未就“应届生”身份进行追问，该表述属于实体提取错误。摘要中“性能测试（最高20万并发）”的描述存在歧义，原文中发言者2在回答“你做过最高的并发是做到多少？”时回答“最高的是最后20万”，可能是指测试中的并发用户数，但摘要未明确单位（如“20万并发用户”），表述不够精确。1.4：摘要将“职业规划表述不够清晰，最初回答‘做老板’，后改称‘踏踏实实干活’”作为风险点，但原文中面试官询问“你写的职业规划是做老板是啥意思？”时，发言者2回答“这个其实是我瞎写的，因为我目前没有什么大的规划，我就想踏踏实实干活”，该回答并非“改称”，而是对“做老板”这一规划的直接解释和澄清，摘要的因果逻辑表述不准确。2.1：摘要缺失了面试中最核心的结论性信息——面试官最终给出的“最高给到12k，15k给不到，如果13k可以接受则安排复试，否则不再考虑”这一关键薪资谈判结果，这是整场面试的实质性结论，属于全局核心遗漏.2.3：摘要中的“能力评估”表格内容多为对面试问答的概括性复述，如“能清晰描述测试用例设计规范”“掌握接口测试（正向/异常）”等，缺乏对候选人表现优劣的深入评判，且部分描述（如“沟通协作”维度）未结合具体面试互动细节，冗余约30%"/>
+            <filter val="1.1：'提议学唱《水手》作为情绪调节尝试'与原文不符，原文中《水手》是来访者此前已学会的歌曲（'你上次放的水手我会唱了'），并非咨询师新提议的任务；2.1：遗漏了来访者关于欧文亚隆存在主义心理学四大终极问题（死亡、自由、孤独、无意义）的讨论内容，这是原文中较重要的哲学探讨环节；2.1：遗漏了来访者明确表达的'未来梦想当一个歌手'的具体职业向往，仅概括为'对音乐有强烈兴趣'"/>
+            <filter val="2.1 核心遗漏：对于住宿的部分没有提及&#10;3.2 小标题合理性：互动与体验部分分类不合理，马队体验可以并入千问的那拉提景区介绍，美食单独作为一个分类呈现&#10;自驾部分应该单独作为一个分类"/>
+            <filter val="1.2：摘要将部分受访者身份归属错误。原文中发言者2明确表示自己是“做当代艺术的”（艺术家），发言者3是“做设计的”，而摘要将其合并归为“当代艺术家/策展人”，未准确区分二人身份；发言者4并非“自由职业设计师”，原文中其称“我是做摄影的”，摘要归纳有偏差；发言者12并非“互联网平台618搞的朋友”，而是电商从业者，发言者13是与其聊工作的同行，摘要将二人合并表述为“与这位互联网平台618搞的朋友”，导致身份混淆。2.1：本次街头采访的核心主题是“深夜工作日外出的原因”，受访者的个人故事和独特回答（如“多邻国打卡1000多天”“阿森纳是冠军”“南昌路最帅调酒师之争”等）是本视频的重要看点，但摘要仅以表格形式概括职业和作息，缺失了这些富有趣味性和个性化的内容，降低了访谈摘要的可读性和传播价值"/>
+            <filter val="2.1 核心遗漏：只分析了候选人的相关信息，面试结果未提及，公司方的信息也没有&#10;2.2 比例失调：对于候选人亮点和风险点的分析都抓住的不算核心矛盾"/>
+            <filter val="2.1 核心遗漏：只分析了候选人的相关信息，面试结果未提及，公司方的信息也没有&#10;关于薪资、学历等关键面试信息都没有提及&#10;2.2 比例失调：对于候选人亮点和风险点的分析都抓住的不算核心矛盾"/>
+            <filter val="1.1: 幻觉，摘要中'情绪反应持续时间：分手后立即产生强烈情绪，持续约1个月'，原文中来访者未明确提及分手到咨询的具体时长，仅提及'最近跟我相处5年的男朋友分手了'，'持续约1个月'为模型自行添加的具体时间数据.。2.1: 全局核心遗漏，原文咨询的核心结论为'靠时间疗愈'和'容易被情绪绑架'，摘要虽提及但未充分强调咨询师对来访者'靠时间''时间还不够'这一核心判断，以及来访者对'时间够不够'的追问（'那多久算时间够'）这一互动关键点，略有遗漏"/>
+            <filter val="2.1 核心遗漏：没有介绍来访的基本背景&#10;3.2 小标题合理性：心理症状是整个核心困扰中所有部分都涉及的，不应该单拎成一个小部分&#10;情绪疏导和共情与支持有概念重叠"/>
+            <filter val="2.1 核心遗漏：没有介绍来访的基本背景&#10;2.2 比例失调：对于咨询干预后来访的改善篇幅过小&#10;3.2 小标题合理性：心理支持和共情与支持有概念重叠"/>
+            <filter val="2.1 核心遗漏：教师对提出问题的解决建议基本未提及&#10;2.3 冗余：家长反馈部分不需要引用家长原话&#10;3.3 分段不合理：对于解决方案的分类太多、太碎，主次结构也不清晰&#10;3.4 内容重复多次：家长反馈没有必要用两个分类提两次"/>
+            <filter val="1.3：摘要中提到“提出需高薪聘请技术骨干但未明确招聘进度”，原文发言者6确实提及“高薪聘用几个作为招牌”，但同时也提到“招收新学员”，摘要仅提及聘请技术骨干，遗漏了“招收新学员”这一并列计划，属于部分实体提取不完整.1.4：摘要中“积分兑换制度（10元=1积分）及消费积分有效期管理方案”表述基本准确，但原文中积分规则由发言者1和发言者6等共同讨论，且明确消费积分每年清零、预存积分永久有效，摘要未区分两类积分，简化了逻辑细节，但未严重扭曲。2.1：全文最核心的讨论成果（开业套餐方案、会员活动、老带新机制、装修风格、积分制度等）在“进度追踪”模块中有所覆盖，但缺少对“男性休息区保留与否”、“VIP客户随行人员免费体验”等几项关键决策的明确记录，且未提炼出任何明确的最终决议或共识，例如套餐是否最终确定、装修风格是否定调等，全局核心结论缺失。2.2：摘要将原文内容结构化呈现，但部分模块（如“营销推广策略”）内容单薄，仅简单罗列，而原文中有大量关于具体套餐细节、促销活动（如398元拉新方案、进店送礼等）的详细讨论，被过度简略，导致比例失调。2.3：全文摘要中“进度追踪”表格内容多为对原文发言的概括，但部分描述仍偏列举式，例如“提出19.9元体验套餐（含...）”、“制定线上线下结合方案：...”等，保留了较多罗列细节，缺乏对核心策略的提炼，冗余约30%。"/>
+            <filter val="2.1 核心遗漏：对于自驾、住宿的部分没有提及&#10;3.2 小标题合理性：与马队互动怎么会属于行程调整呢"/>
+            <filter val="1.3：摘要中“投资公司于2016年5月10日提交再审答辩状时附带7份附件”表述准确，但原文中发言者1明确说明附件二、三、六、七为“不作为新证据提交，只是供法院参考”，摘要未区分哪些是证据哪些是参考资料，存在轻微实体提取不完整。2.1：摘要缺失了法庭辩论环节中最核心的法律争点——即“雇佣救助合同是否适用海商法183条按比例分摊规则”这一双方交锋最激烈的焦点，仅以表格形式简单罗列双方观点，未体现投资公司关于“人命救助应扣减50%报酬”的关键抗辩，也未体现南海救助局关于“海商法但书条款仅适用于人命酬金”的核心辩论意见，属于全局核心遗漏.2.2：摘要将大量篇幅用于罗列“证据提交情况”“质证意见”“法官询问要点”等程序性内容，而法庭辩论阶段的法律争议内核被压缩为简表，比例略有失调"/>
+            <filter val="识别模板正确。2.1:对'社工与社区协调困难'细节提炼略浅；3.1:个别标点略不规范"/>
+            <filter val="识别模板正确。2.1:对'线上线下融合'核心议题提炼略浅；3.1:个别标点略不规范"/>
+            <filter val="识别模板正确。2.1:对面试具体问答细节提炼略浅,部分技术问题未充分呈现；3.1:个别标点略不规范"/>
+            <filter val="2.1 核心遗漏：没有把问题的关键现状和解决措施列完整&#10;3.2 小标题合理性：归类业主提出的问题不应该概括为信息同步&#10;4.3 层级逻辑极其混乱：每个问题都应该按照问题现状-物业回应-解决措施的逻辑排列，现在的整个顺序是乱的"/>
+            <filter val="1.1：事实错误，跨课程联合宣传是发言者1提的，摘要中写的发言者3和4&#10;2.1：细节遗漏：招生策略中缺少“先抓住孩子，再抓父母”，舞蹈班缺少对不同需求的区分"/>
+            <filter val="2.1 核心遗漏：没有把当前产品类型的所有阻塞问题列出来&#10;没有把管理层对于问题处理方案的决策列出来&#10;4.3 层级逻辑极其混乱：不同产品类型的格式不一样"/>
+            <filter val="1.1 幻觉：编造原文不存在的具体参数，略微严重&#10;2.1 比例失调：原文虽然归类产品发布但主要是纪录片内容，摘要侧重了产品，倒也没什么问题"/>
+            <filter val="1.1：'5年测试伪装应届生'为原文标题/摘要性描述，候选人实际自述为应届生，模型未在概况中说明这一身份争议的来源（标题描述 vs 候选人自述），可能造成误解；1.3：候选人期望薪资原文仅记录为'20'，模型直接解读为'20K'，原文未明确单位，存在数值单位推断；2.1：遗漏面试官对候选人'真的是应届生吗'的质疑及候选人'可能我长得有点显老'的回应这一关键互动细节（虽在综合素质中提及但未在概况中体现）；2.1：遗漏候选人'不行，这是原则性问题'的完整语境（针对薪资20K被压低后的回应），模型在沟通协作维度仅简略提及"/>
+            <filter val="2.1 细节遗漏，遗漏部分受访者观点的细节&#10;2.2 从100万到7位数（百万）不等 表述不通顺"/>
+            <filter val="2.1 核心遗漏：提取金句时没头没尾的，只看截取部分不明白想表达什么&#10;3.2 小标题合理性：童年早于车祸残疾的经历怎么能属于人生选择和创作态度呢&#10;关于电影创作和对人生的理解，与第一个大分类有重叠&#10;4.3 层级逻辑极其混乱：不理解是以什么逻辑顺序呈现的，不同部分之间的界限不清晰，重叠部分也很多"/>
+            <filter val="1.1: 幻觉，摘要中'改进计划'第3条'财务与人力资源部门需解决薪酬问题：优先解决员工工资拖欠问题，确保当月工资按时发放'等表述，原文总经理明确表示资金紧张，但并未承诺'确保当月工资按时发放'，而是提出'会向董事长反应资金问题'，此措辞属于过度承诺.摘要中'改进计划'第3条'建立资金使用审批绿色通道'，原文完全未提及此概念，属于凭空捏造。1.3: 实体提取错误，摘要中'酒店已拖欠员工工资达半年'，原文后勤保障部发言人5提到'半年没开工资啦'，但总经理并未确认该时长，且可能为特定部门情况，摘要将其作为全局事实陈述，存在归因偏差。1.4: 逻辑错乱，摘要中'责任推诿现象：各部门存在将问题上交推卸责任的情况'，原文仅总经理提到'别把问题甩给我'，但后勤部门发言人5明确表示已多次打报告申请资金未获批准，并非推诿而是流程受阻，摘要将其简单归为'推诿'与原文语境不符。2.1: 全局核心遗漏，会议核心为酒店停业整顿原因分析及责任追究，原文总经理强调了消防、食品、服务等多方面问题，且后勤部门回应了资金不足导致整改困难，但摘要的'改进计划'完全未提及如何协调资金短缺这一根本矛盾（总经理承认资金紧张，后勤强调无钱整改），缺失核心症结讨论。2.2: 比例失调，摘要中'改进计划'部分占篇幅较大，但原文后半部分讨论的核心'资金短缺与工资拖欠'仅在'不足事项'中一笔带过，未充分体现后勤部门对无钱整改的反驳及双方争论，重点略偏"/>
+            <filter val="识别模板错误：应为'采访记录'，模型识别为'心理咨询'。原文为采访对话，受访者疑似姜思达（发言者2提及'下面请姜思达发言'），非心理咨询关系；1.1：咨询小结中'布置的家庭作业是记录一周内在不同社交场景中的自我评价内容'、'下次咨询将重点讨论如何区分自我保护与自我限制的界限'均为模型捏造，原文未提及任何家庭作业或下次咨询计划；1.1：'来访者承认通过回避社交活动可以缓解不适'与原文不符，原文是发言者1提到'通过不参加任何活动得到了全然的改变'，且这是作为歌手保护嗓子的客观原因，非回避社交的应对策略；2.1：因模板选错，未按采访记录模板（访谈概述、访谈详细记录、关键引语与金句）组织内容，遗漏了原文中具有传播价值的关键引语，如'如果没有什么关系是永恒的，你还敢投入吗？'、'如果太大声会显得我太冒进，太小声，别人会听不见'等；2.1：未识别出受访者身份（姜思达）及采访背景"/>
+            <filter val="识别模板错误：应为'总结复盘会'，模型识别为'团队例会'，导致整体结构（复盘目标与结果概况、亮点事项、不足事项、改进计划）缺失；1.1：协作需求中'计划在12月中旬前完成初步沟通'、'确保宣传覆盖率达100%'为模型捏造，原文未提及具体时间节点和覆盖率指标；2.1：遗漏事故科核心数据（事故率同比下降7.5%、酒驾肇事占1%、突发事故占22.3%、车辆故障占17.5%、高峰期事故占40%多）；2.1：遗漏事故科提出的4点改进建议具体内容（加大打击惩罚力度、偏僻路口增加投入、高峰期增加人力辅助、与安全科合作）；2.1：遗漏二大队关于开发区超速、闯红灯、工程车超载等核心问题的具体分析"/>
+            <filter val="2.1：遗漏了发言者1关于歌手身份与保护嗓子的内容、在朋友群聊中&quot;没有什么原因坐在那就是很想哭&quot;的具体例子、&quot;安静不是一个选择，安静是你唯一的能力&quot;等关键表述；关键引语准确无误，访谈结构清晰"/>
+            <filter val="2.1:对'青春期沟通'这一核心话题提炼略浅；3.1:个别标点略不规范"/>
+            <filter val="2.1:对'社工与社区协调困难'这一细节提炼略浅；3.1:个别标点略不规范"/>
+            <filter val="2.1:对'线上线下融合'这一核心议题提炼略显不足；3.1:个别标点略不规范"/>
+            <filter val="1.1：发布会日期&quot;2020年7月23日&quot;在原文中未明确提及，原文仅提及该日期为许某某被刑事拘留时间，模型将其作为发布会日期属推断/捏造；2.1：遗漏了许某某&quot;自1987年开始先后在绍兴、上海等地从事鱼粉和养殖生意&quot;的背景信息；整体案件时间线、侦查数据、当事人信息梳理准确完整"/>
+            <filter val="1.1: 幻觉，摘要中'最终决议'部分将多个讨论中的提议直接定性为'确定'或'实施'的决议，例如'确定19.9元体验套餐'、'实施满1000元办卡政策'、'采用粉色/紫色主色调'等，但原文为多人发言的商讨场景，发言者1多次以'可以''也行'等词汇表示认可，并未明确宣布最终决议，摘要将讨论内容转化为正式决策属于过度确定性表述.1.3: 实体提取错误，摘要中'韩国冰醇小气泡'原文为'韩国冰韩韩国冰醇小气包儿'（应为'韩国冰醇小气泡'，但原文有口误），模型提取为'韩国冰醇小气泡'基本正确，但'PTD电子光疗'原文为'P T D电子光疗'，提取无大问题；但摘要将'外延排毒刮痧'写为'外延排毒刮痧'（原文为'外延排毒刮痧'）摘要中'充值500元赠100积分、充值1000元赠200积分'，原文发言人2表述为'充五百赠一百''充一千赠两百'，但发言人3提到'充三百赠一百充五百赠两百'，摘要只取部分发言者提议并未区分来源，且将'赠金额'误解为'赠积分'，原文积分与赠金为两套体系（积分按消费金额累积，赠金为充值赠送），摘要混淆。1.4: 逻辑错乱，摘要'遗留问题第5条：促销活动的时间范围（如365元/年方案的具体有效期）需确定'，原文发言人5提出365元/年方案时明确为'全年美容'，时间范围本身已明确（一年），摘要将其列为'需确定'的逻辑与实际不符。2.1: 全局核心遗漏，会议开场明确讨论议题包括'优惠政策、套餐内容、员工工资、装修风格'，摘要虽涵盖了套餐、会员、装修、积分等，但遗漏了员工工资讨论（发言人1开头提及），且对'装修风格'的讨论较简略（未提及灯具、布帘等细节）2.3: 冗余，摘要中'方案陈述'表格和'最终决议'、'遗留问题'存在大量重复内容（同一套餐、活动在多个部分重复描述），冗余内容超过30%"/>
+            <filter val="1.2 事实错误：缺货的是低档烟，不是高档烟&#10;2.1 核心遗漏：工作内容部分没有囊括所有的问题&#10;没有把管理层对于问题处理方案的决策列出来"/>
+            <filter val="1.2：摘要将“后勤保障部”负责人（发言者5）的强烈反驳意见简单归为“反馈”，并称其“申请资金解决工资发放问题”，但原文中发言者5明确表示“半年没开工资”、“我是没告你们”，态度激烈，摘要弱化了这种对抗性，且未体现其对总经理批评的直接反驳，属于观点提取不准确。1.3：摘要中“总经理需要各部门提交详细的整改方案和时间节点”属于捏造，原文中总经理并未提出此要求；同时，“餐饮部需要检查厨房用具安全，特别是天然气使用安全”是总经理在会议后期提出的，并非餐饮部自己反馈的计划，摘要错误地将该要求归为餐饮部的“后续计划”，属于归属错误。1.4：摘要将停业整顿的主要原因归为“消防器材过期、电路老化、食材采购及厨房安全”，但原文中总经理明确指出“主要还是一些咱们酒店内部处理的这一些问题”，涵盖消防、设备、客户投诉、员工消极怠工等多个方面，且后勤保障部负责人指出根本原因是资金短缺导致设备无法更换，摘要未准确反映这一核心因果关系，简化了复杂的责任归属。2.1：整场会议最核心的议题是总经理追责、各部门自我辩护与相互指责，以及因资金短缺导致的整改困境，但摘要完全缺失“各部门责任推诿”这一核心矛盾，也未提及总经理“该撤的撤、该降的降”等严厉表态，以及后勤保障部对资金问题的直接挑战，导致核心冲突与会议性质被严重弱化，属于全局核心遗漏。2.2：摘要将大量篇幅用于罗列各部门“问题-现状-后续计划”的表格，但这些内容多为对原文发言的机械拆分，而真正关键的互动交锋（如后勤保障部对总经理的当面反驳、餐饮部与后勤部关于食材质量的争执）被一笔带过或完全忽略，比例严重失调。2.3：摘要中的表格内容多为对原文口语的复述式概括，例如“消防通道堆放杂物、消防器材过期生锈”、“半年未发工资”等，缺乏更高层次的提炼，冗余超过50%"/>
+            <filter val="1.2：摘要中“咨询师指出来访者可能存在‘撒娇’倾向”描述不够准确，原文中咨询师说的是“你别从这个世界撒娇”、“你快点哄哄我就不哄我”，是咨询师对来访者反复说“但是”这一行为的解读，并非直接指出来访者存在撒娇倾向，表述略有偏差。2.1：摘要整体覆盖了咨询的核心议题和咨询师的主要干预技术，但遗漏了部分重要细节：咨询师明确指出来访者“脑子极混乱”、“容易被情绪绑架，被感觉绑架”、“感觉不加验证”，这些对来访者思维模式的描述是咨询师做出“靠时间”结论的关键依据，摘要未充分提取"/>
+            <filter val="2.1：遗漏了咨询师分享自身19岁经历（山东卫视首席主持人）、萨老师哥伦比亚大学心理学硕士背景、具体合唱歌曲《水手》、录有声书建议等细节；整体内容准确，干预技术归纳合理"/>
+            <filter val="1.2：销售技巧探讨中&quot;发言者6指出需通过细节服务（如送小礼品、递茶水）提升客户好感度&quot;实际为发言者3所述（原文发言者3提到&quot;送小礼品递茶水等细节部分&quot;）；2.1：&quot;达成共识与解决方案&quot;和&quot;未决分歧与后续探索&quot;部分内容为模型自行归纳，原文为开放式讨论，未明确达成共识或列出后续探索事项，属轻度拔高"/>
+            <filter val="1.1 事实错误，口才班需求支持与原文不一致；1.2 待协调事项负责人、对接人原文并未明确。2.1 细节遗漏，遗漏学生匹配度、先转孩子再抓父母的策略；"/>
+            <filter val="1.1 部分对接人、负责人幻觉，但还好；2.1 待协调事项部分内容与前文重复"/>
+            <filter val="2.1 核心遗漏：没有把问题的关键现状和解决措施列完整&#10;3.2 小标题合理性：归类业主提出的问题不应该概括为信息同步&#10;物业对于问题的回应和解决方案不应该概括为达成共识&#10;4.3 层级逻辑极其混乱：每个问题都应该按照问题现状-物业回应-解决措施的逻辑排列，现在要对应问题和相应的方案很困难"/>
+            <filter val="2.1：遗漏嫌疑人作案动机（因家庭生活矛盾对来某某产生不满，于7月5日凌晨在家中趁来某某熟睡之际将其杀害、分尸后分散抛弃）这一关键案件事实；2.1：遗漏化粪池筛查的具体时间（7月22日下午）、恶劣工作条件（40度高温、连续奋战25小时）等关键侦查细节；2.1：遗漏被害人基本信息（51岁、杭州某公司保洁员）；2.1：遗漏嫌疑人背景（1987年起在绍兴、上海从事鱼粉和养殖生意，2018年到杭州工作）；2.1：遗漏对小区1075户人家开展询问走访的规模信息"/>
+            <filter val="识别模板正确。2.1:对'家庭氛围压抑'背景信息提炼略浅；3.1:个别标点略不规范"/>
+            <filter val="1.4 逻辑错乱：净化器需求增加应该属于家电区的工作内容&#10;2.1 核心遗漏：工作内容部分没有囊括所有的问题&#10;没有把管理层对于问题处理方案的决策列出来"/>
+            <filter val="1.4：综合素质中&quot;对技术问题有持续学习的态度&quot;与原文候选人表达&quot;再久我真的要废了，搞不动了&quot;、&quot;不想搞了，累了累了&quot;的疲惫态度不符，存在逻辑判断偏差；2.1：原文为40+分钟长面试，模型遗漏了UniApp多端编译、Docker部署、Nacos服务注册发现、Sharding JDBC分库分表、CPU 100%事故（序列号写错入库几百亿）、本地压测QPS 1500、银信通项目对接第三方支付等多个技术话题讨论；项目经验评估过于简略"/>
+            <filter val="2.1 核心遗漏：双方的共识没有提及&#10;4.3 层级逻辑极其混乱：应该按照核心论点-立论框架-支撑论据的逻辑顺序排列"/>
+            <filter val="2.1 核心遗漏：对于论据的概括避重就轻，比如出现平台，没有强调主要出现在非权利中心这一关键论据&#10;双方的共识没有强调&#10;没有论述为什么反方胜利&#10;4.3 层级逻辑极其混乱：应该按照核心论点-立论框架-支撑论据的逻辑顺序排列"/>
+            <filter val="1.1 幻觉：：只有一个原告&#10;1.2 事实错误：要求追加被告的是法院方，不是原告&#10;2.1 核心遗漏：只写了第一、第二被告，这些分别代表什么人和公司没有提及&#10;出庭情况没有提及&#10;只有质证，没有提及被质疑的证据具体是什么"/>
+            <filter val="1.1：改进计划中&quot;19:00-23:00时段增派警力&quot;在原文中未提及，原文仅说&quot;晚上&quot;，具体时段属捏造；1.1：&quot;每月至少开展一次中小学交通安全公开课&quot;的频率原文未提及；1.1：&quot;结合测速设备强化夜间管控&quot;原文未明确提及测速设备；2.1：遗漏了事故科关于事故原因的具体数据（酒驾占1%、突发事故22.3%、车辆故障17.5%、高峰期40%+）及事故科提出的三点改进建议（加大酒驾打击力度、偏僻路口增加投入、高峰期增加人力辅助）"/>
+            <filter val="2.1：遗漏了关键背景信息&quot;5年测试伪装应届生，面试官质疑是不是应届王&quot;，这是整个面试的核心语境和疑点；2.1：遗漏了候选人&quot;可能我长得有点显老&quot;的回应、视频面试形式（&quot;面试官可以看见到我吗&quot;）；2.1：遗漏了SQL优化中&quot;避免使用不等于号、索引不超过6个&quot;等具体细节；候选人OSI模型回答存在ASR错误但模型未予纠正说明"/>
+            <filter val="2.1 核心遗漏：只写了国际公司作为第二被告，其他被告的身份没有提及&#10;出庭情况没有提及&#10;只有质证，没有提及被质疑的证据具体是什么&#10;4.3 层级逻辑极其混乱：被告没有按照第一被告往下的顺序排列，可读性比较差"/>
+          </filters>
+        </filterColumn>
+      </autoFilter>
+    </autofilterInfo>
+  </sheetItem>
+  <sheetItem sheetStid="14">
+    <filterData filterID="AK20210901JXNSXO17933749"/>
+    <autofilterInfo filterID="AK20210901JXNSXO17933749">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N168"/>
+    </autofilterInfo>
+  </sheetItem>
+  <sheetItem sheetStid="16">
+    <filterData filterID="AK20210901JXNSXO17933749"/>
+    <filterData filterID="AK20210901JXNSXO16981454"/>
+    <autofilterInfo filterID="AK20210901JXNSXO16981454">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:S168"/>
+    </autofilterInfo>
+    <autofilterInfo filterID="AK20210901JXNSXO17933749">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:S168"/>
+    </autofilterInfo>
+  </sheetItem>
+</autofilters>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <woSheetsProps>
+    <woSheetProps sheetStid="6" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="4" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="5" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="3" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="7" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="9" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="10" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="11" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="12" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="14" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="16" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="18" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+  </woSheetsProps>
+  <woBookProps>
+    <bookSettings isFilterShared="0" coreConquerUserId="" isAutoUpdatePaused="0" filterType="user" isMergeTasksAutoUpdate="0" isInserPicAsAttachment="0"/>
+  </woBookProps>
+</woProps>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="6"/>
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="4"/>
+  <pixelatorList sheetStid="5"/>
+  <pixelatorList sheetStid="3"/>
+  <pixelatorList sheetStid="7"/>
+  <pixelatorList sheetStid="9"/>
+  <pixelatorList sheetStid="10"/>
+  <pixelatorList sheetStid="11"/>
+  <pixelatorList sheetStid="12"/>
+  <pixelatorList sheetStid="14"/>
+  <pixelatorList sheetStid="16"/>
+  <pixelatorList sheetStid="18"/>
+  <pixelatorList sheetStid="19"/>
+</pixelators>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5662047-3127-477A-AC3A-1D340467FB41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>